--- a/11_Planificacion/Cronograma_Tesis.xlsx
+++ b/11_Planificacion/Cronograma_Tesis.xlsx
@@ -45,12 +45,11 @@
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <numFmts count="5">
-    <numFmt numFmtId="164" formatCode="yyyy-mm-dd"/>
-    <numFmt numFmtId="165" formatCode="dd-mmm"/>
-    <numFmt numFmtId="166" formatCode="dddd"/>
-    <numFmt numFmtId="167" formatCode="0.0"/>
-    <numFmt numFmtId="168" formatCode="dd-mmm-yy"/>
+  <numFmts count="4">
+    <numFmt numFmtId="164" formatCode="dd-mmm"/>
+    <numFmt numFmtId="165" formatCode="dddd"/>
+    <numFmt numFmtId="166" formatCode="0.0"/>
+    <numFmt numFmtId="167" formatCode="dd-mmm-yy"/>
   </numFmts>
   <fonts count="12">
     <font>
@@ -157,7 +156,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="22">
+  <cellXfs count="27">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="2" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
@@ -180,18 +179,29 @@
     <xf numFmtId="0" fontId="7" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment vertical="top" wrapText="1"/>
     </xf>
+    <xf numFmtId="164" fontId="7" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment vertical="top" wrapText="1"/>
+    </xf>
     <xf numFmtId="165" fontId="7" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment vertical="top" wrapText="1"/>
     </xf>
     <xf numFmtId="166" fontId="7" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment vertical="top" wrapText="1"/>
     </xf>
-    <xf numFmtId="167" fontId="7" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="167" fontId="7" fillId="0" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="165" fontId="7" fillId="0" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="164" fontId="7" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment vertical="top" wrapText="1"/>
     </xf>
-    <xf numFmtId="168" fontId="7" fillId="0" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="166" fontId="7" fillId="0" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="7" fillId="0" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="165" fontId="7" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="166" fontId="7" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="167" fontId="7" fillId="0" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="165" fontId="7" fillId="0" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0" hidden="0"/>
@@ -1070,10 +1080,10 @@
           <t>S7-T01</t>
         </is>
       </c>
-      <c r="B6" s="16" t="n">
+      <c r="B6" s="22" t="n">
         <v>46348</v>
       </c>
-      <c r="C6" s="17">
+      <c r="C6" s="23">
         <f>B6</f>
         <v/>
       </c>
@@ -1102,10 +1112,10 @@
           <t>Prueba de acceso de cada usuario</t>
         </is>
       </c>
-      <c r="I6" s="18" t="n">
+      <c r="I6" s="24" t="n">
         <v>1</v>
       </c>
-      <c r="J6" s="16" t="n"/>
+      <c r="J6" s="22" t="n"/>
       <c r="K6" s="15" t="inlineStr">
         <is>
           <t>Pendiente</t>
@@ -1128,10 +1138,10 @@
           <t>S7-T02</t>
         </is>
       </c>
-      <c r="B7" s="16" t="n">
+      <c r="B7" s="22" t="n">
         <v>46349</v>
       </c>
-      <c r="C7" s="17">
+      <c r="C7" s="23">
         <f>B7</f>
         <v/>
       </c>
@@ -1160,10 +1170,10 @@
           <t>Lista de asistentes</t>
         </is>
       </c>
-      <c r="I7" s="18" t="n">
+      <c r="I7" s="24" t="n">
         <v>1.5</v>
       </c>
-      <c r="J7" s="16" t="n"/>
+      <c r="J7" s="22" t="n"/>
       <c r="K7" s="15" t="inlineStr">
         <is>
           <t>Pendiente</t>
@@ -1186,10 +1196,10 @@
           <t>S7-T03</t>
         </is>
       </c>
-      <c r="B8" s="16" t="n">
+      <c r="B8" s="22" t="n">
         <v>46350</v>
       </c>
-      <c r="C8" s="17">
+      <c r="C8" s="23">
         <f>B8</f>
         <v/>
       </c>
@@ -1218,10 +1228,10 @@
           <t>Eventos sin errores</t>
         </is>
       </c>
-      <c r="I8" s="18" t="n">
+      <c r="I8" s="24" t="n">
         <v>1</v>
       </c>
-      <c r="J8" s="16" t="n"/>
+      <c r="J8" s="22" t="n"/>
       <c r="K8" s="15" t="inlineStr">
         <is>
           <t>Pendiente</t>
@@ -1244,10 +1254,10 @@
           <t>S7-T04</t>
         </is>
       </c>
-      <c r="B9" s="16" t="n">
+      <c r="B9" s="22" t="n">
         <v>46350</v>
       </c>
-      <c r="C9" s="17">
+      <c r="C9" s="23">
         <f>B9</f>
         <v/>
       </c>
@@ -1276,10 +1286,10 @@
           <t>Solo datos con registro de procedencia</t>
         </is>
       </c>
-      <c r="I9" s="18" t="n">
+      <c r="I9" s="24" t="n">
         <v>2</v>
       </c>
-      <c r="J9" s="16" t="n"/>
+      <c r="J9" s="22" t="n"/>
       <c r="K9" s="15" t="inlineStr">
         <is>
           <t>Pendiente</t>
@@ -1302,10 +1312,10 @@
           <t>S7-T05</t>
         </is>
       </c>
-      <c r="B10" s="16" t="n">
+      <c r="B10" s="22" t="n">
         <v>46351</v>
       </c>
-      <c r="C10" s="17">
+      <c r="C10" s="23">
         <f>B10</f>
         <v/>
       </c>
@@ -1334,10 +1344,10 @@
           <t>Revisada a diario</t>
         </is>
       </c>
-      <c r="I10" s="18" t="n">
+      <c r="I10" s="24" t="n">
         <v>0.5</v>
       </c>
-      <c r="J10" s="16" t="n"/>
+      <c r="J10" s="22" t="n"/>
       <c r="K10" s="15" t="inlineStr">
         <is>
           <t>Pendiente</t>
@@ -1360,10 +1370,10 @@
           <t>S7-T06</t>
         </is>
       </c>
-      <c r="B11" s="16" t="n">
+      <c r="B11" s="22" t="n">
         <v>46351</v>
       </c>
-      <c r="C11" s="17">
+      <c r="C11" s="23">
         <f>B11</f>
         <v/>
       </c>
@@ -1392,10 +1402,10 @@
           <t>Observaciones cerradas</t>
         </is>
       </c>
-      <c r="I11" s="18" t="n">
+      <c r="I11" s="24" t="n">
         <v>1.5</v>
       </c>
-      <c r="J11" s="16" t="n"/>
+      <c r="J11" s="22" t="n"/>
       <c r="K11" s="15" t="inlineStr">
         <is>
           <t>Pendiente</t>
@@ -1418,10 +1428,10 @@
           <t>S7-T07</t>
         </is>
       </c>
-      <c r="B12" s="16" t="n">
+      <c r="B12" s="22" t="n">
         <v>46351</v>
       </c>
-      <c r="C12" s="17">
+      <c r="C12" s="23">
         <f>B12</f>
         <v/>
       </c>
@@ -1450,10 +1460,10 @@
           <t>Capítulo completo</t>
         </is>
       </c>
-      <c r="I12" s="18" t="n">
+      <c r="I12" s="24" t="n">
         <v>2</v>
       </c>
-      <c r="J12" s="16" t="n"/>
+      <c r="J12" s="22" t="n"/>
       <c r="K12" s="15" t="inlineStr">
         <is>
           <t>Pendiente</t>
@@ -1476,10 +1486,10 @@
           <t>S7-T08</t>
         </is>
       </c>
-      <c r="B13" s="16" t="n">
+      <c r="B13" s="22" t="n">
         <v>46352</v>
       </c>
-      <c r="C13" s="17">
+      <c r="C13" s="23">
         <f>B13</f>
         <v/>
       </c>
@@ -1508,10 +1518,10 @@
           <t>Revisada a diario</t>
         </is>
       </c>
-      <c r="I13" s="18" t="n">
+      <c r="I13" s="24" t="n">
         <v>0.5</v>
       </c>
-      <c r="J13" s="16" t="n"/>
+      <c r="J13" s="22" t="n"/>
       <c r="K13" s="15" t="inlineStr">
         <is>
           <t>Pendiente</t>
@@ -1534,10 +1544,10 @@
           <t>S7-T09</t>
         </is>
       </c>
-      <c r="B14" s="16" t="n">
+      <c r="B14" s="22" t="n">
         <v>46352</v>
       </c>
-      <c r="C14" s="17">
+      <c r="C14" s="23">
         <f>B14</f>
         <v/>
       </c>
@@ -1566,10 +1576,10 @@
           <t>Observaciones cerradas</t>
         </is>
       </c>
-      <c r="I14" s="18" t="n">
+      <c r="I14" s="24" t="n">
         <v>2</v>
       </c>
-      <c r="J14" s="16" t="n"/>
+      <c r="J14" s="22" t="n"/>
       <c r="K14" s="15" t="inlineStr">
         <is>
           <t>Pendiente</t>
@@ -1592,10 +1602,10 @@
           <t>S7-T10</t>
         </is>
       </c>
-      <c r="B15" s="16" t="n">
+      <c r="B15" s="22" t="n">
         <v>46353</v>
       </c>
-      <c r="C15" s="17">
+      <c r="C15" s="23">
         <f>B15</f>
         <v/>
       </c>
@@ -1624,10 +1634,10 @@
           <t>Revisada a diario</t>
         </is>
       </c>
-      <c r="I15" s="18" t="n">
+      <c r="I15" s="24" t="n">
         <v>0.5</v>
       </c>
-      <c r="J15" s="16" t="n"/>
+      <c r="J15" s="22" t="n"/>
       <c r="K15" s="15" t="inlineStr">
         <is>
           <t>Pendiente</t>
@@ -1650,10 +1660,10 @@
           <t>S7-T11</t>
         </is>
       </c>
-      <c r="B16" s="16" t="n">
+      <c r="B16" s="22" t="n">
         <v>46353</v>
       </c>
-      <c r="C16" s="17">
+      <c r="C16" s="23">
         <f>B16</f>
         <v/>
       </c>
@@ -1682,10 +1692,10 @@
           <t>Revisado una vez</t>
         </is>
       </c>
-      <c r="I16" s="18" t="n">
+      <c r="I16" s="24" t="n">
         <v>2</v>
       </c>
-      <c r="J16" s="16" t="n"/>
+      <c r="J16" s="22" t="n"/>
       <c r="K16" s="15" t="inlineStr">
         <is>
           <t>Pendiente</t>
@@ -1708,10 +1718,10 @@
           <t>S7-T12</t>
         </is>
       </c>
-      <c r="B17" s="16" t="n">
+      <c r="B17" s="22" t="n">
         <v>46354</v>
       </c>
-      <c r="C17" s="17">
+      <c r="C17" s="23">
         <f>B17</f>
         <v/>
       </c>
@@ -1740,10 +1750,10 @@
           <t>Revisada</t>
         </is>
       </c>
-      <c r="I17" s="18" t="n">
+      <c r="I17" s="24" t="n">
         <v>3</v>
       </c>
-      <c r="J17" s="16" t="n"/>
+      <c r="J17" s="22" t="n"/>
       <c r="K17" s="15" t="inlineStr">
         <is>
           <t>Pendiente</t>
@@ -1766,10 +1776,10 @@
           <t>S7-T13</t>
         </is>
       </c>
-      <c r="B18" s="16" t="n">
+      <c r="B18" s="22" t="n">
         <v>46354</v>
       </c>
-      <c r="C18" s="17">
+      <c r="C18" s="23">
         <f>B18</f>
         <v/>
       </c>
@@ -1798,10 +1808,10 @@
           <t>Diego lo leyó</t>
         </is>
       </c>
-      <c r="I18" s="18" t="n">
+      <c r="I18" s="24" t="n">
         <v>0.5</v>
       </c>
-      <c r="J18" s="16" t="n"/>
+      <c r="J18" s="22" t="n"/>
       <c r="K18" s="15" t="inlineStr">
         <is>
           <t>Pendiente</t>
@@ -1824,10 +1834,10 @@
           <t>S7-T14</t>
         </is>
       </c>
-      <c r="B19" s="16" t="n">
+      <c r="B19" s="22" t="n">
         <v>46355</v>
       </c>
-      <c r="C19" s="17">
+      <c r="C19" s="23">
         <f>B19</f>
         <v/>
       </c>
@@ -1856,10 +1866,10 @@
           <t>El informe del domingo (21:00) sale con la sección nueva</t>
         </is>
       </c>
-      <c r="I19" s="18" t="n">
+      <c r="I19" s="24" t="n">
         <v>1</v>
       </c>
-      <c r="J19" s="16" t="n"/>
+      <c r="J19" s="22" t="n"/>
       <c r="K19" s="15" t="inlineStr">
         <is>
           <t>Pendiente</t>
@@ -2062,10 +2072,10 @@
           <t>S8-T01</t>
         </is>
       </c>
-      <c r="B6" s="16" t="n">
+      <c r="B6" s="22" t="n">
         <v>46356</v>
       </c>
-      <c r="C6" s="17">
+      <c r="C6" s="23">
         <f>B6</f>
         <v/>
       </c>
@@ -2094,10 +2104,10 @@
           <t>Cada decisión con criterio</t>
         </is>
       </c>
-      <c r="I6" s="18" t="n">
+      <c r="I6" s="24" t="n">
         <v>1.5</v>
       </c>
-      <c r="J6" s="16" t="n"/>
+      <c r="J6" s="22" t="n"/>
       <c r="K6" s="15" t="inlineStr">
         <is>
           <t>Pendiente</t>
@@ -2120,10 +2130,10 @@
           <t>S8-T02</t>
         </is>
       </c>
-      <c r="B7" s="16" t="n">
+      <c r="B7" s="22" t="n">
         <v>46356</v>
       </c>
-      <c r="C7" s="17">
+      <c r="C7" s="23">
         <f>B7</f>
         <v/>
       </c>
@@ -2152,10 +2162,10 @@
           <t>Revisada</t>
         </is>
       </c>
-      <c r="I7" s="18" t="n">
+      <c r="I7" s="24" t="n">
         <v>0.5</v>
       </c>
-      <c r="J7" s="16" t="n"/>
+      <c r="J7" s="22" t="n"/>
       <c r="K7" s="15" t="inlineStr">
         <is>
           <t>Pendiente</t>
@@ -2178,10 +2188,10 @@
           <t>S8-T03</t>
         </is>
       </c>
-      <c r="B8" s="16" t="n">
+      <c r="B8" s="22" t="n">
         <v>46356</v>
       </c>
-      <c r="C8" s="17">
+      <c r="C8" s="23">
         <f>B8</f>
         <v/>
       </c>
@@ -2210,10 +2220,10 @@
           <t>Integra los flujos TO-BE</t>
         </is>
       </c>
-      <c r="I8" s="18" t="n">
+      <c r="I8" s="24" t="n">
         <v>2</v>
       </c>
-      <c r="J8" s="16" t="n"/>
+      <c r="J8" s="22" t="n"/>
       <c r="K8" s="15" t="inlineStr">
         <is>
           <t>Pendiente</t>
@@ -2236,10 +2246,10 @@
           <t>S8-T04</t>
         </is>
       </c>
-      <c r="B9" s="16" t="n">
+      <c r="B9" s="22" t="n">
         <v>46357</v>
       </c>
-      <c r="C9" s="17">
+      <c r="C9" s="23">
         <f>B9</f>
         <v/>
       </c>
@@ -2268,10 +2278,10 @@
           <t>Coincide con la prueba de concepto</t>
         </is>
       </c>
-      <c r="I9" s="18" t="n">
+      <c r="I9" s="24" t="n">
         <v>1.5</v>
       </c>
-      <c r="J9" s="16" t="n"/>
+      <c r="J9" s="22" t="n"/>
       <c r="K9" s="15" t="inlineStr">
         <is>
           <t>Pendiente</t>
@@ -2294,10 +2304,10 @@
           <t>S8-T05</t>
         </is>
       </c>
-      <c r="B10" s="16" t="n">
+      <c r="B10" s="22" t="n">
         <v>46357</v>
       </c>
-      <c r="C10" s="17">
+      <c r="C10" s="23">
         <f>B10</f>
         <v/>
       </c>
@@ -2326,10 +2336,10 @@
           <t>Revisada</t>
         </is>
       </c>
-      <c r="I10" s="18" t="n">
+      <c r="I10" s="24" t="n">
         <v>0.5</v>
       </c>
-      <c r="J10" s="16" t="n"/>
+      <c r="J10" s="22" t="n"/>
       <c r="K10" s="15" t="inlineStr">
         <is>
           <t>Pendiente</t>
@@ -2352,10 +2362,10 @@
           <t>S8-T06</t>
         </is>
       </c>
-      <c r="B11" s="16" t="n">
+      <c r="B11" s="22" t="n">
         <v>46357</v>
       </c>
-      <c r="C11" s="17">
+      <c r="C11" s="23">
         <f>B11</f>
         <v/>
       </c>
@@ -2384,10 +2394,10 @@
           <t>Integra el modelo financiero</t>
         </is>
       </c>
-      <c r="I11" s="18" t="n">
+      <c r="I11" s="24" t="n">
         <v>2</v>
       </c>
-      <c r="J11" s="16" t="n"/>
+      <c r="J11" s="22" t="n"/>
       <c r="K11" s="15" t="inlineStr">
         <is>
           <t>Pendiente</t>
@@ -2410,10 +2420,10 @@
           <t>S8-T07</t>
         </is>
       </c>
-      <c r="B12" s="16" t="n">
+      <c r="B12" s="22" t="n">
         <v>46358</v>
       </c>
-      <c r="C12" s="17">
+      <c r="C12" s="23">
         <f>B12</f>
         <v/>
       </c>
@@ -2442,10 +2452,10 @@
           <t>Revisado por Víctor</t>
         </is>
       </c>
-      <c r="I12" s="18" t="n">
+      <c r="I12" s="24" t="n">
         <v>1.5</v>
       </c>
-      <c r="J12" s="16" t="n"/>
+      <c r="J12" s="22" t="n"/>
       <c r="K12" s="15" t="inlineStr">
         <is>
           <t>Pendiente</t>
@@ -2468,10 +2478,10 @@
           <t>S8-T08</t>
         </is>
       </c>
-      <c r="B13" s="16" t="n">
+      <c r="B13" s="22" t="n">
         <v>46358</v>
       </c>
-      <c r="C13" s="17">
+      <c r="C13" s="23">
         <f>B13</f>
         <v/>
       </c>
@@ -2500,10 +2510,10 @@
           <t>Revisada</t>
         </is>
       </c>
-      <c r="I13" s="18" t="n">
+      <c r="I13" s="24" t="n">
         <v>0.5</v>
       </c>
-      <c r="J13" s="16" t="n"/>
+      <c r="J13" s="22" t="n"/>
       <c r="K13" s="15" t="inlineStr">
         <is>
           <t>Pendiente</t>
@@ -2526,10 +2536,10 @@
           <t>S8-T09</t>
         </is>
       </c>
-      <c r="B14" s="16" t="n">
+      <c r="B14" s="22" t="n">
         <v>46358</v>
       </c>
-      <c r="C14" s="17">
+      <c r="C14" s="23">
         <f>B14</f>
         <v/>
       </c>
@@ -2558,10 +2568,10 @@
           <t>Integra normativa y riesgos</t>
         </is>
       </c>
-      <c r="I14" s="18" t="n">
+      <c r="I14" s="24" t="n">
         <v>2</v>
       </c>
-      <c r="J14" s="16" t="n"/>
+      <c r="J14" s="22" t="n"/>
       <c r="K14" s="15" t="inlineStr">
         <is>
           <t>Pendiente</t>
@@ -2584,10 +2594,10 @@
           <t>S8-T10</t>
         </is>
       </c>
-      <c r="B15" s="16" t="n">
+      <c r="B15" s="22" t="n">
         <v>46359</v>
       </c>
-      <c r="C15" s="17">
+      <c r="C15" s="23">
         <f>B15</f>
         <v/>
       </c>
@@ -2616,10 +2626,10 @@
           <t>Resultado por caso</t>
         </is>
       </c>
-      <c r="I15" s="18" t="n">
+      <c r="I15" s="24" t="n">
         <v>1.5</v>
       </c>
-      <c r="J15" s="16" t="n"/>
+      <c r="J15" s="22" t="n"/>
       <c r="K15" s="15" t="inlineStr">
         <is>
           <t>Pendiente</t>
@@ -2642,10 +2652,10 @@
           <t>S8-T11</t>
         </is>
       </c>
-      <c r="B16" s="16" t="n">
+      <c r="B16" s="22" t="n">
         <v>46359</v>
       </c>
-      <c r="C16" s="17">
+      <c r="C16" s="23">
         <f>B16</f>
         <v/>
       </c>
@@ -2674,10 +2684,10 @@
           <t>Revisada</t>
         </is>
       </c>
-      <c r="I16" s="18" t="n">
+      <c r="I16" s="24" t="n">
         <v>0.5</v>
       </c>
-      <c r="J16" s="16" t="n"/>
+      <c r="J16" s="22" t="n"/>
       <c r="K16" s="15" t="inlineStr">
         <is>
           <t>Pendiente</t>
@@ -2700,10 +2710,10 @@
           <t>S8-T12</t>
         </is>
       </c>
-      <c r="B17" s="16" t="n">
+      <c r="B17" s="22" t="n">
         <v>46359</v>
       </c>
-      <c r="C17" s="17">
+      <c r="C17" s="23">
         <f>B17</f>
         <v/>
       </c>
@@ -2732,10 +2742,10 @@
           <t>Comentarios enviados</t>
         </is>
       </c>
-      <c r="I17" s="18" t="n">
+      <c r="I17" s="24" t="n">
         <v>2</v>
       </c>
-      <c r="J17" s="16" t="n"/>
+      <c r="J17" s="22" t="n"/>
       <c r="K17" s="15" t="inlineStr">
         <is>
           <t>Pendiente</t>
@@ -2758,10 +2768,10 @@
           <t>S8-T13</t>
         </is>
       </c>
-      <c r="B18" s="16" t="n">
+      <c r="B18" s="22" t="n">
         <v>46360</v>
       </c>
-      <c r="C18" s="17">
+      <c r="C18" s="23">
         <f>B18</f>
         <v/>
       </c>
@@ -2790,10 +2800,10 @@
           <t>Un usuario de Torvesa lo puede seguir</t>
         </is>
       </c>
-      <c r="I18" s="18" t="n">
+      <c r="I18" s="24" t="n">
         <v>1.5</v>
       </c>
-      <c r="J18" s="16" t="n"/>
+      <c r="J18" s="22" t="n"/>
       <c r="K18" s="15" t="inlineStr">
         <is>
           <t>Pendiente</t>
@@ -2816,10 +2826,10 @@
           <t>S8-T14</t>
         </is>
       </c>
-      <c r="B19" s="16" t="n">
+      <c r="B19" s="22" t="n">
         <v>46360</v>
       </c>
-      <c r="C19" s="17">
+      <c r="C19" s="23">
         <f>B19</f>
         <v/>
       </c>
@@ -2848,10 +2858,10 @@
           <t>Capítulo completo</t>
         </is>
       </c>
-      <c r="I19" s="18" t="n">
+      <c r="I19" s="24" t="n">
         <v>2</v>
       </c>
-      <c r="J19" s="16" t="n"/>
+      <c r="J19" s="22" t="n"/>
       <c r="K19" s="15" t="inlineStr">
         <is>
           <t>Pendiente</t>
@@ -2874,10 +2884,10 @@
           <t>S8-T15</t>
         </is>
       </c>
-      <c r="B20" s="16" t="n">
+      <c r="B20" s="22" t="n">
         <v>46361</v>
       </c>
-      <c r="C20" s="17">
+      <c r="C20" s="23">
         <f>B20</f>
         <v/>
       </c>
@@ -2906,10 +2916,10 @@
           <t>Hash anotado</t>
         </is>
       </c>
-      <c r="I20" s="18" t="n">
+      <c r="I20" s="24" t="n">
         <v>2</v>
       </c>
-      <c r="J20" s="16" t="n"/>
+      <c r="J20" s="22" t="n"/>
       <c r="K20" s="15" t="inlineStr">
         <is>
           <t>Pendiente</t>
@@ -2932,10 +2942,10 @@
           <t>S8-T16</t>
         </is>
       </c>
-      <c r="B21" s="16" t="n">
+      <c r="B21" s="22" t="n">
         <v>46361</v>
       </c>
-      <c r="C21" s="17">
+      <c r="C21" s="23">
         <f>B21</f>
         <v/>
       </c>
@@ -2964,10 +2974,10 @@
           <t>Iguales a los de la línea base</t>
         </is>
       </c>
-      <c r="I21" s="18" t="n">
+      <c r="I21" s="24" t="n">
         <v>2</v>
       </c>
-      <c r="J21" s="16" t="n"/>
+      <c r="J21" s="22" t="n"/>
       <c r="K21" s="15" t="inlineStr">
         <is>
           <t>Pendiente</t>
@@ -2990,10 +3000,10 @@
           <t>S8-T17</t>
         </is>
       </c>
-      <c r="B22" s="16" t="n">
+      <c r="B22" s="22" t="n">
         <v>46362</v>
       </c>
-      <c r="C22" s="17">
+      <c r="C22" s="23">
         <f>B22</f>
         <v/>
       </c>
@@ -3022,10 +3032,10 @@
           <t>Leídos por el otro</t>
         </is>
       </c>
-      <c r="I22" s="18" t="n">
+      <c r="I22" s="24" t="n">
         <v>1</v>
       </c>
-      <c r="J22" s="16" t="n"/>
+      <c r="J22" s="22" t="n"/>
       <c r="K22" s="15" t="inlineStr">
         <is>
           <t>Pendiente</t>
@@ -3048,10 +3058,10 @@
           <t>S8-T18</t>
         </is>
       </c>
-      <c r="B23" s="16" t="n">
+      <c r="B23" s="22" t="n">
         <v>46362</v>
       </c>
-      <c r="C23" s="17">
+      <c r="C23" s="23">
         <f>B23</f>
         <v/>
       </c>
@@ -3080,10 +3090,10 @@
           <t>El informe del domingo (21:00) sale con la sección nueva</t>
         </is>
       </c>
-      <c r="I23" s="18" t="n">
+      <c r="I23" s="24" t="n">
         <v>1</v>
       </c>
-      <c r="J23" s="16" t="n"/>
+      <c r="J23" s="22" t="n"/>
       <c r="K23" s="15" t="inlineStr">
         <is>
           <t>Pendiente</t>
@@ -3286,10 +3296,10 @@
           <t>S9-T01</t>
         </is>
       </c>
-      <c r="B6" s="16" t="n">
+      <c r="B6" s="22" t="n">
         <v>46363</v>
       </c>
-      <c r="C6" s="17">
+      <c r="C6" s="23">
         <f>B6</f>
         <v/>
       </c>
@@ -3318,10 +3328,10 @@
           <t>Cada aplicación registrada</t>
         </is>
       </c>
-      <c r="I6" s="18" t="n">
+      <c r="I6" s="24" t="n">
         <v>2</v>
       </c>
-      <c r="J6" s="16" t="n"/>
+      <c r="J6" s="22" t="n"/>
       <c r="K6" s="15" t="inlineStr">
         <is>
           <t>Pendiente</t>
@@ -3344,10 +3354,10 @@
           <t>S9-T02</t>
         </is>
       </c>
-      <c r="B7" s="16" t="n">
+      <c r="B7" s="22" t="n">
         <v>46364</v>
       </c>
-      <c r="C7" s="17">
+      <c r="C7" s="23">
         <f>B7</f>
         <v/>
       </c>
@@ -3376,10 +3386,10 @@
           <t>Cada aplicación registrada</t>
         </is>
       </c>
-      <c r="I7" s="18" t="n">
+      <c r="I7" s="24" t="n">
         <v>2</v>
       </c>
-      <c r="J7" s="16" t="n"/>
+      <c r="J7" s="22" t="n"/>
       <c r="K7" s="15" t="inlineStr">
         <is>
           <t>Pendiente</t>
@@ -3402,10 +3412,10 @@
           <t>S9-T03</t>
         </is>
       </c>
-      <c r="B8" s="16" t="n">
+      <c r="B8" s="22" t="n">
         <v>46365</v>
       </c>
-      <c r="C8" s="17">
+      <c r="C8" s="23">
         <f>B8</f>
         <v/>
       </c>
@@ -3434,10 +3444,10 @@
           <t>Cada aplicación registrada</t>
         </is>
       </c>
-      <c r="I8" s="18" t="n">
+      <c r="I8" s="24" t="n">
         <v>2</v>
       </c>
-      <c r="J8" s="16" t="n"/>
+      <c r="J8" s="22" t="n"/>
       <c r="K8" s="15" t="inlineStr">
         <is>
           <t>Pendiente</t>
@@ -3460,10 +3470,10 @@
           <t>S9-T04</t>
         </is>
       </c>
-      <c r="B9" s="16" t="n">
+      <c r="B9" s="22" t="n">
         <v>46366</v>
       </c>
-      <c r="C9" s="17">
+      <c r="C9" s="23">
         <f>B9</f>
         <v/>
       </c>
@@ -3492,10 +3502,10 @@
           <t>Pruebas del borrador + tamaño del efecto</t>
         </is>
       </c>
-      <c r="I9" s="18" t="n">
+      <c r="I9" s="24" t="n">
         <v>2</v>
       </c>
-      <c r="J9" s="16" t="n"/>
+      <c r="J9" s="22" t="n"/>
       <c r="K9" s="15" t="inlineStr">
         <is>
           <t>Pendiente</t>
@@ -3518,10 +3528,10 @@
           <t>S9-T05</t>
         </is>
       </c>
-      <c r="B10" s="16" t="n">
+      <c r="B10" s="22" t="n">
         <v>46366</v>
       </c>
-      <c r="C10" s="17">
+      <c r="C10" s="23">
         <f>B10</f>
         <v/>
       </c>
@@ -3550,10 +3560,10 @@
           <t>Escenarios reproducibles</t>
         </is>
       </c>
-      <c r="I10" s="18" t="n">
+      <c r="I10" s="24" t="n">
         <v>2</v>
       </c>
-      <c r="J10" s="16" t="n"/>
+      <c r="J10" s="22" t="n"/>
       <c r="K10" s="15" t="inlineStr">
         <is>
           <t>Pendiente</t>
@@ -3576,10 +3586,10 @@
           <t>S9-T06</t>
         </is>
       </c>
-      <c r="B11" s="16" t="n">
+      <c r="B11" s="22" t="n">
         <v>46367</v>
       </c>
-      <c r="C11" s="17">
+      <c r="C11" s="23">
         <f>B11</f>
         <v/>
       </c>
@@ -3608,10 +3618,10 @@
           <t>Revisados con Diego</t>
         </is>
       </c>
-      <c r="I11" s="18" t="n">
+      <c r="I11" s="24" t="n">
         <v>2</v>
       </c>
-      <c r="J11" s="16" t="n"/>
+      <c r="J11" s="22" t="n"/>
       <c r="K11" s="15" t="inlineStr">
         <is>
           <t>Pendiente</t>
@@ -3634,10 +3644,10 @@
           <t>S9-T07</t>
         </is>
       </c>
-      <c r="B12" s="16" t="n">
+      <c r="B12" s="22" t="n">
         <v>46367</v>
       </c>
-      <c r="C12" s="17">
+      <c r="C12" s="23">
         <f>B12</f>
         <v/>
       </c>
@@ -3666,10 +3676,10 @@
           <t>Legibles y con título</t>
         </is>
       </c>
-      <c r="I12" s="18" t="n">
+      <c r="I12" s="24" t="n">
         <v>2</v>
       </c>
-      <c r="J12" s="16" t="n"/>
+      <c r="J12" s="22" t="n"/>
       <c r="K12" s="15" t="inlineStr">
         <is>
           <t>Pendiente</t>
@@ -3692,10 +3702,10 @@
           <t>S9-T08</t>
         </is>
       </c>
-      <c r="B13" s="16" t="n">
+      <c r="B13" s="22" t="n">
         <v>46368</v>
       </c>
-      <c r="C13" s="17">
+      <c r="C13" s="23">
         <f>B13</f>
         <v/>
       </c>
@@ -3724,10 +3734,10 @@
           <t>Capítulo completo</t>
         </is>
       </c>
-      <c r="I13" s="18" t="n">
+      <c r="I13" s="24" t="n">
         <v>3</v>
       </c>
-      <c r="J13" s="16" t="n"/>
+      <c r="J13" s="22" t="n"/>
       <c r="K13" s="15" t="inlineStr">
         <is>
           <t>Pendiente</t>
@@ -3750,10 +3760,10 @@
           <t>S9-T09</t>
         </is>
       </c>
-      <c r="B14" s="16" t="n">
+      <c r="B14" s="22" t="n">
         <v>46368</v>
       </c>
-      <c r="C14" s="17">
+      <c r="C14" s="23">
         <f>B14</f>
         <v/>
       </c>
@@ -3782,10 +3792,10 @@
           <t>Comentarios enviados</t>
         </is>
       </c>
-      <c r="I14" s="18" t="n">
+      <c r="I14" s="24" t="n">
         <v>2</v>
       </c>
-      <c r="J14" s="16" t="n"/>
+      <c r="J14" s="22" t="n"/>
       <c r="K14" s="15" t="inlineStr">
         <is>
           <t>Pendiente</t>
@@ -3808,10 +3818,10 @@
           <t>S9-T10</t>
         </is>
       </c>
-      <c r="B15" s="16" t="n">
+      <c r="B15" s="22" t="n">
         <v>46369</v>
       </c>
-      <c r="C15" s="17">
+      <c r="C15" s="23">
         <f>B15</f>
         <v/>
       </c>
@@ -3840,10 +3850,10 @@
           <t>El informe del domingo (21:00) sale con la sección nueva</t>
         </is>
       </c>
-      <c r="I15" s="18" t="n">
+      <c r="I15" s="24" t="n">
         <v>1</v>
       </c>
-      <c r="J15" s="16" t="n"/>
+      <c r="J15" s="22" t="n"/>
       <c r="K15" s="15" t="inlineStr">
         <is>
           <t>Pendiente</t>
@@ -4046,10 +4056,10 @@
           <t>S10-T01</t>
         </is>
       </c>
-      <c r="B6" s="16" t="n">
+      <c r="B6" s="22" t="n">
         <v>46370</v>
       </c>
-      <c r="C6" s="17">
+      <c r="C6" s="23">
         <f>B6</f>
         <v/>
       </c>
@@ -4078,10 +4088,10 @@
           <t>Acuse de recibo</t>
         </is>
       </c>
-      <c r="I6" s="18" t="n">
+      <c r="I6" s="24" t="n">
         <v>1</v>
       </c>
-      <c r="J6" s="16" t="n"/>
+      <c r="J6" s="22" t="n"/>
       <c r="K6" s="15" t="inlineStr">
         <is>
           <t>Pendiente</t>
@@ -4104,10 +4114,10 @@
           <t>S10-T02</t>
         </is>
       </c>
-      <c r="B7" s="16" t="n">
+      <c r="B7" s="22" t="n">
         <v>46370</v>
       </c>
-      <c r="C7" s="17">
+      <c r="C7" s="23">
         <f>B7</f>
         <v/>
       </c>
@@ -4136,10 +4146,10 @@
           <t>Sin errores</t>
         </is>
       </c>
-      <c r="I7" s="18" t="n">
+      <c r="I7" s="24" t="n">
         <v>2</v>
       </c>
-      <c r="J7" s="16" t="n"/>
+      <c r="J7" s="22" t="n"/>
       <c r="K7" s="15" t="inlineStr">
         <is>
           <t>Pendiente</t>
@@ -4162,10 +4172,10 @@
           <t>S10-T03</t>
         </is>
       </c>
-      <c r="B8" s="16" t="n">
+      <c r="B8" s="22" t="n">
         <v>46371</v>
       </c>
-      <c r="C8" s="17">
+      <c r="C8" s="23">
         <f>B8</f>
         <v/>
       </c>
@@ -4194,10 +4204,10 @@
           <t>Acta corta</t>
         </is>
       </c>
-      <c r="I8" s="18" t="n">
+      <c r="I8" s="24" t="n">
         <v>1</v>
       </c>
-      <c r="J8" s="16" t="n"/>
+      <c r="J8" s="22" t="n"/>
       <c r="K8" s="15" t="inlineStr">
         <is>
           <t>Pendiente</t>
@@ -4220,10 +4230,10 @@
           <t>S10-T04</t>
         </is>
       </c>
-      <c r="B9" s="16" t="n">
+      <c r="B9" s="22" t="n">
         <v>46372</v>
       </c>
-      <c r="C9" s="17">
+      <c r="C9" s="23">
         <f>B9</f>
         <v/>
       </c>
@@ -4252,10 +4262,10 @@
           <t>Observaciones cerradas</t>
         </is>
       </c>
-      <c r="I9" s="18" t="n">
+      <c r="I9" s="24" t="n">
         <v>2</v>
       </c>
-      <c r="J9" s="16" t="n"/>
+      <c r="J9" s="22" t="n"/>
       <c r="K9" s="15" t="inlineStr">
         <is>
           <t>Pendiente</t>
@@ -4278,10 +4288,10 @@
           <t>S10-T05</t>
         </is>
       </c>
-      <c r="B10" s="16" t="n">
+      <c r="B10" s="22" t="n">
         <v>46373</v>
       </c>
-      <c r="C10" s="17">
+      <c r="C10" s="23">
         <f>B10</f>
         <v/>
       </c>
@@ -4310,10 +4320,10 @@
           <t>Acta corta</t>
         </is>
       </c>
-      <c r="I10" s="18" t="n">
+      <c r="I10" s="24" t="n">
         <v>1</v>
       </c>
-      <c r="J10" s="16" t="n"/>
+      <c r="J10" s="22" t="n"/>
       <c r="K10" s="15" t="inlineStr">
         <is>
           <t>Pendiente</t>
@@ -4336,10 +4346,10 @@
           <t>S10-T06</t>
         </is>
       </c>
-      <c r="B11" s="16" t="n">
+      <c r="B11" s="22" t="n">
         <v>46374</v>
       </c>
-      <c r="C11" s="17">
+      <c r="C11" s="23">
         <f>B11</f>
         <v/>
       </c>
@@ -4368,10 +4378,10 @@
           <t>Todos los capítulos + bibliografía verificada</t>
         </is>
       </c>
-      <c r="I11" s="18" t="n">
+      <c r="I11" s="24" t="n">
         <v>2</v>
       </c>
-      <c r="J11" s="16" t="n"/>
+      <c r="J11" s="22" t="n"/>
       <c r="K11" s="15" t="inlineStr">
         <is>
           <t>Pendiente</t>
@@ -4394,10 +4404,10 @@
           <t>S10-T07</t>
         </is>
       </c>
-      <c r="B12" s="16" t="n">
+      <c r="B12" s="22" t="n">
         <v>46375</v>
       </c>
-      <c r="C12" s="17">
+      <c r="C12" s="23">
         <f>B12</f>
         <v/>
       </c>
@@ -4426,10 +4436,10 @@
           <t>Lectura completa hecha</t>
         </is>
       </c>
-      <c r="I12" s="18" t="n">
+      <c r="I12" s="24" t="n">
         <v>3</v>
       </c>
-      <c r="J12" s="16" t="n"/>
+      <c r="J12" s="22" t="n"/>
       <c r="K12" s="15" t="inlineStr">
         <is>
           <t>Pendiente</t>
@@ -4452,10 +4462,10 @@
           <t>S10-T08</t>
         </is>
       </c>
-      <c r="B13" s="16" t="n">
+      <c r="B13" s="22" t="n">
         <v>46376</v>
       </c>
-      <c r="C13" s="17">
+      <c r="C13" s="23">
         <f>B13</f>
         <v/>
       </c>
@@ -4484,10 +4494,10 @@
           <t>El informe del domingo (21:00) sale con la sección nueva</t>
         </is>
       </c>
-      <c r="I13" s="18" t="n">
+      <c r="I13" s="24" t="n">
         <v>1</v>
       </c>
-      <c r="J13" s="16" t="n"/>
+      <c r="J13" s="22" t="n"/>
       <c r="K13" s="15" t="inlineStr">
         <is>
           <t>Pendiente</t>
@@ -4690,10 +4700,10 @@
           <t>Holgura-T01</t>
         </is>
       </c>
-      <c r="B6" s="16" t="n">
+      <c r="B6" s="22" t="n">
         <v>46378</v>
       </c>
-      <c r="C6" s="17">
+      <c r="C6" s="23">
         <f>B6</f>
         <v/>
       </c>
@@ -4722,10 +4732,10 @@
           <t>0 citas sin ficha</t>
         </is>
       </c>
-      <c r="I6" s="18" t="n">
+      <c r="I6" s="24" t="n">
         <v>1.5</v>
       </c>
-      <c r="J6" s="16" t="n"/>
+      <c r="J6" s="22" t="n"/>
       <c r="K6" s="15" t="inlineStr">
         <is>
           <t>Pendiente</t>
@@ -4748,10 +4758,10 @@
           <t>Holgura-T02</t>
         </is>
       </c>
-      <c r="B7" s="16" t="n">
+      <c r="B7" s="22" t="n">
         <v>46379</v>
       </c>
-      <c r="C7" s="17">
+      <c r="C7" s="23">
         <f>B7</f>
         <v/>
       </c>
@@ -4780,10 +4790,10 @@
           <t>Índice correcto</t>
         </is>
       </c>
-      <c r="I7" s="18" t="n">
+      <c r="I7" s="24" t="n">
         <v>1.5</v>
       </c>
-      <c r="J7" s="16" t="n"/>
+      <c r="J7" s="22" t="n"/>
       <c r="K7" s="15" t="inlineStr">
         <is>
           <t>Pendiente</t>
@@ -4806,10 +4816,10 @@
           <t>Holgura-T03</t>
         </is>
       </c>
-      <c r="B8" s="16" t="n">
+      <c r="B8" s="22" t="n">
         <v>46382</v>
       </c>
-      <c r="C8" s="17">
+      <c r="C8" s="23">
         <f>B8</f>
         <v/>
       </c>
@@ -4838,10 +4848,10 @@
           <t>0 citas sin ficha</t>
         </is>
       </c>
-      <c r="I8" s="18" t="n">
+      <c r="I8" s="24" t="n">
         <v>2</v>
       </c>
-      <c r="J8" s="16" t="n"/>
+      <c r="J8" s="22" t="n"/>
       <c r="K8" s="15" t="inlineStr">
         <is>
           <t>Pendiente</t>
@@ -4864,10 +4874,10 @@
           <t>Holgura-T04</t>
         </is>
       </c>
-      <c r="B9" s="16" t="n">
+      <c r="B9" s="22" t="n">
         <v>46385</v>
       </c>
-      <c r="C9" s="17">
+      <c r="C9" s="23">
         <f>B9</f>
         <v/>
       </c>
@@ -4896,10 +4906,10 @@
           <t>Formato APA en todas</t>
         </is>
       </c>
-      <c r="I9" s="18" t="n">
+      <c r="I9" s="24" t="n">
         <v>2</v>
       </c>
-      <c r="J9" s="16" t="n"/>
+      <c r="J9" s="22" t="n"/>
       <c r="K9" s="15" t="inlineStr">
         <is>
           <t>Pendiente</t>
@@ -4922,10 +4932,10 @@
           <t>Holgura-T05</t>
         </is>
       </c>
-      <c r="B10" s="16" t="n">
+      <c r="B10" s="22" t="n">
         <v>46386</v>
       </c>
-      <c r="C10" s="17">
+      <c r="C10" s="23">
         <f>B10</f>
         <v/>
       </c>
@@ -4954,10 +4964,10 @@
           <t>Numeradas y citadas</t>
         </is>
       </c>
-      <c r="I10" s="18" t="n">
+      <c r="I10" s="24" t="n">
         <v>1.5</v>
       </c>
-      <c r="J10" s="16" t="n"/>
+      <c r="J10" s="22" t="n"/>
       <c r="K10" s="15" t="inlineStr">
         <is>
           <t>Pendiente</t>
@@ -4980,10 +4990,10 @@
           <t>Holgura-T06</t>
         </is>
       </c>
-      <c r="B11" s="16" t="n">
+      <c r="B11" s="22" t="n">
         <v>46389</v>
       </c>
-      <c r="C11" s="17">
+      <c r="C11" s="23">
         <f>B11</f>
         <v/>
       </c>
@@ -5012,10 +5022,10 @@
           <t>Lista cerrada</t>
         </is>
       </c>
-      <c r="I11" s="18" t="n">
+      <c r="I11" s="24" t="n">
         <v>3</v>
       </c>
-      <c r="J11" s="16" t="n"/>
+      <c r="J11" s="22" t="n"/>
       <c r="K11" s="15" t="inlineStr">
         <is>
           <t>Pendiente</t>
@@ -5218,10 +5228,10 @@
           <t>Entrega-T01</t>
         </is>
       </c>
-      <c r="B6" s="16" t="n">
+      <c r="B6" s="22" t="n">
         <v>46391</v>
       </c>
-      <c r="C6" s="17">
+      <c r="C6" s="23">
         <f>B6</f>
         <v/>
       </c>
@@ -5250,10 +5260,10 @@
           <t>Acuse de recibo</t>
         </is>
       </c>
-      <c r="I6" s="18" t="n">
+      <c r="I6" s="24" t="n">
         <v>1</v>
       </c>
-      <c r="J6" s="16" t="n"/>
+      <c r="J6" s="22" t="n"/>
       <c r="K6" s="15" t="inlineStr">
         <is>
           <t>Pendiente</t>
@@ -5276,10 +5286,10 @@
           <t>Entrega-T02</t>
         </is>
       </c>
-      <c r="B7" s="16" t="n">
+      <c r="B7" s="22" t="n">
         <v>46393</v>
       </c>
-      <c r="C7" s="17">
+      <c r="C7" s="23">
         <f>B7</f>
         <v/>
       </c>
@@ -5308,10 +5318,10 @@
           <t>Observaciones cerradas</t>
         </is>
       </c>
-      <c r="I7" s="18" t="n">
+      <c r="I7" s="24" t="n">
         <v>2</v>
       </c>
-      <c r="J7" s="16" t="n"/>
+      <c r="J7" s="22" t="n"/>
       <c r="K7" s="15" t="inlineStr">
         <is>
           <t>Pendiente</t>
@@ -5334,10 +5344,10 @@
           <t>Entrega-T03</t>
         </is>
       </c>
-      <c r="B8" s="16" t="n">
+      <c r="B8" s="22" t="n">
         <v>46394</v>
       </c>
-      <c r="C8" s="17">
+      <c r="C8" s="23">
         <f>B8</f>
         <v/>
       </c>
@@ -5366,10 +5376,10 @@
           <t>Firma</t>
         </is>
       </c>
-      <c r="I8" s="18" t="n">
+      <c r="I8" s="24" t="n">
         <v>1</v>
       </c>
-      <c r="J8" s="16" t="n"/>
+      <c r="J8" s="22" t="n"/>
       <c r="K8" s="15" t="inlineStr">
         <is>
           <t>Pendiente</t>
@@ -5392,10 +5402,10 @@
           <t>Entrega-T04</t>
         </is>
       </c>
-      <c r="B9" s="16" t="n">
+      <c r="B9" s="22" t="n">
         <v>46395</v>
       </c>
-      <c r="C9" s="17">
+      <c r="C9" s="23">
         <f>B9</f>
         <v/>
       </c>
@@ -5424,10 +5434,10 @@
           <t>Comprobante recibido</t>
         </is>
       </c>
-      <c r="I9" s="18" t="n">
+      <c r="I9" s="24" t="n">
         <v>1</v>
       </c>
-      <c r="J9" s="16" t="n"/>
+      <c r="J9" s="22" t="n"/>
       <c r="K9" s="15" t="inlineStr">
         <is>
           <t>Pendiente</t>
@@ -5630,10 +5640,10 @@
           <t>Defensa-T01</t>
         </is>
       </c>
-      <c r="B6" s="16" t="n">
+      <c r="B6" s="22" t="n">
         <v>46399</v>
       </c>
-      <c r="C6" s="17">
+      <c r="C6" s="23">
         <f>B6</f>
         <v/>
       </c>
@@ -5662,10 +5672,10 @@
           <t>Aprobado por los dos</t>
         </is>
       </c>
-      <c r="I6" s="18" t="n">
+      <c r="I6" s="24" t="n">
         <v>2</v>
       </c>
-      <c r="J6" s="16" t="n"/>
+      <c r="J6" s="22" t="n"/>
       <c r="K6" s="15" t="inlineStr">
         <is>
           <t>Pendiente</t>
@@ -5688,10 +5698,10 @@
           <t>Defensa-T02</t>
         </is>
       </c>
-      <c r="B7" s="16" t="n">
+      <c r="B7" s="22" t="n">
         <v>46410</v>
       </c>
-      <c r="C7" s="17">
+      <c r="C7" s="23">
         <f>B7</f>
         <v/>
       </c>
@@ -5720,10 +5730,10 @@
           <t>Cada uno sabe su parte y la del otro</t>
         </is>
       </c>
-      <c r="I7" s="18" t="n">
+      <c r="I7" s="24" t="n">
         <v>3</v>
       </c>
-      <c r="J7" s="16" t="n"/>
+      <c r="J7" s="22" t="n"/>
       <c r="K7" s="15" t="inlineStr">
         <is>
           <t>Pendiente</t>
@@ -5746,10 +5756,10 @@
           <t>Defensa-T03</t>
         </is>
       </c>
-      <c r="B8" s="16" t="n">
+      <c r="B8" s="22" t="n">
         <v>46417</v>
       </c>
-      <c r="C8" s="17">
+      <c r="C8" s="23">
         <f>B8</f>
         <v/>
       </c>
@@ -5778,10 +5788,10 @@
           <t>Simulacro cronometrado</t>
         </is>
       </c>
-      <c r="I8" s="18" t="n">
+      <c r="I8" s="24" t="n">
         <v>3</v>
       </c>
-      <c r="J8" s="16" t="n"/>
+      <c r="J8" s="22" t="n"/>
       <c r="K8" s="15" t="inlineStr">
         <is>
           <t>Pendiente</t>
@@ -5804,10 +5814,10 @@
           <t>Defensa-T04</t>
         </is>
       </c>
-      <c r="B9" s="16" t="n">
+      <c r="B9" s="22" t="n">
         <v>46424</v>
       </c>
-      <c r="C9" s="17">
+      <c r="C9" s="23">
         <f>B9</f>
         <v/>
       </c>
@@ -5836,10 +5846,10 @@
           <t>Ambos responden todo el banco</t>
         </is>
       </c>
-      <c r="I9" s="18" t="n">
+      <c r="I9" s="24" t="n">
         <v>3</v>
       </c>
-      <c r="J9" s="16" t="n"/>
+      <c r="J9" s="22" t="n"/>
       <c r="K9" s="15" t="inlineStr">
         <is>
           <t>Pendiente</t>
@@ -5862,10 +5872,10 @@
           <t>Defensa-T05</t>
         </is>
       </c>
-      <c r="B10" s="16" t="n">
+      <c r="B10" s="22" t="n">
         <v>46427</v>
       </c>
-      <c r="C10" s="17">
+      <c r="C10" s="23">
         <f>B10</f>
         <v/>
       </c>
@@ -5894,10 +5904,10 @@
           <t>Aprobada</t>
         </is>
       </c>
-      <c r="I10" s="18" t="n">
+      <c r="I10" s="24" t="n">
         <v>2</v>
       </c>
-      <c r="J10" s="16" t="n"/>
+      <c r="J10" s="22" t="n"/>
       <c r="K10" s="15" t="inlineStr">
         <is>
           <t>Pendiente</t>
@@ -6758,6 +6768,7 @@
         <v/>
       </c>
     </row>
+    <row r="4"/>
     <row r="5" ht="30" customHeight="1">
       <c r="A5" s="14" t="inlineStr">
         <is>
@@ -6836,10 +6847,10 @@
           <t>S1-T01</t>
         </is>
       </c>
-      <c r="B6" s="16" t="n">
+      <c r="B6" s="22" t="n">
         <v>46307</v>
       </c>
-      <c r="C6" s="17">
+      <c r="C6" s="23">
         <f>B6</f>
         <v/>
       </c>
@@ -6868,13 +6879,15 @@
           <t>Las 5 preguntas tienen respuesta (sí / no / pendiente)</t>
         </is>
       </c>
-      <c r="I6" s="18" t="n">
+      <c r="I6" s="24" t="n">
         <v>1</v>
       </c>
-      <c r="J6" s="16" t="n"/>
+      <c r="J6" s="22" t="n">
+        <v>46307</v>
+      </c>
       <c r="K6" s="15" t="inlineStr">
         <is>
-          <t>Pendiente</t>
+          <t>Hecho</t>
         </is>
       </c>
       <c r="L6" s="15">
@@ -6886,7 +6899,11 @@
           <t>S1-07 (#7)</t>
         </is>
       </c>
-      <c r="N6" s="15" t="inlineStr"/>
+      <c r="N6" s="15" t="inlineStr">
+        <is>
+          <t>Víctor conversó con la tutora: sin objeciones a los 5 puntos (lo dijo Víctor el 18-oct). Falta confirmar la fecha de entrega (D5)</t>
+        </is>
+      </c>
     </row>
     <row r="7">
       <c r="A7" s="15" t="inlineStr">
@@ -6894,10 +6911,10 @@
           <t>S1-T02</t>
         </is>
       </c>
-      <c r="B7" s="16" t="n">
+      <c r="B7" s="22" t="n">
         <v>46307</v>
       </c>
-      <c r="C7" s="17">
+      <c r="C7" s="23">
         <f>B7</f>
         <v/>
       </c>
@@ -6926,13 +6943,13 @@
           <t>Acta con decisiones y fechas</t>
         </is>
       </c>
-      <c r="I7" s="18" t="n">
+      <c r="I7" s="24" t="n">
         <v>0.5</v>
       </c>
-      <c r="J7" s="16" t="n"/>
+      <c r="J7" s="22" t="n"/>
       <c r="K7" s="15" t="inlineStr">
         <is>
-          <t>Pendiente</t>
+          <t>Movido</t>
         </is>
       </c>
       <c r="L7" s="15">
@@ -6944,7 +6961,11 @@
           <t>S1-07 (#7)</t>
         </is>
       </c>
-      <c r="N7" s="15" t="inlineStr"/>
+      <c r="N7" s="15" t="inlineStr">
+        <is>
+          <t>Víctor decidió hacer el acta más adelante (18-oct)</t>
+        </is>
+      </c>
     </row>
     <row r="8">
       <c r="A8" s="15" t="inlineStr">
@@ -6952,10 +6973,10 @@
           <t>S1-T03</t>
         </is>
       </c>
-      <c r="B8" s="16" t="n">
+      <c r="B8" s="22" t="n">
         <v>46307</v>
       </c>
-      <c r="C8" s="17">
+      <c r="C8" s="23">
         <f>B8</f>
         <v/>
       </c>
@@ -6984,13 +7005,13 @@
           <t>Copia del correo enviado</t>
         </is>
       </c>
-      <c r="I8" s="18" t="n">
+      <c r="I8" s="24" t="n">
         <v>0.5</v>
       </c>
-      <c r="J8" s="16" t="n"/>
+      <c r="J8" s="22" t="n"/>
       <c r="K8" s="15" t="inlineStr">
         <is>
-          <t>Pendiente</t>
+          <t>Movido</t>
         </is>
       </c>
       <c r="L8" s="15">
@@ -7002,7 +7023,11 @@
           <t>S1-05 (#5)</t>
         </is>
       </c>
-      <c r="N8" s="15" t="inlineStr"/>
+      <c r="N8" s="15" t="inlineStr">
+        <is>
+          <t>Diego se encarga de conseguir la información de Torvesa (decisión de Víctor, 18-oct)</t>
+        </is>
+      </c>
     </row>
     <row r="9">
       <c r="A9" s="15" t="inlineStr">
@@ -7010,10 +7035,10 @@
           <t>S1-T04</t>
         </is>
       </c>
-      <c r="B9" s="16" t="n">
+      <c r="B9" s="22" t="n">
         <v>46307</v>
       </c>
-      <c r="C9" s="17">
+      <c r="C9" s="23">
         <f>B9</f>
         <v/>
       </c>
@@ -7042,13 +7067,13 @@
           <t>El commit de prueba aparece en GitHub</t>
         </is>
       </c>
-      <c r="I9" s="18" t="n">
+      <c r="I9" s="24" t="n">
         <v>1</v>
       </c>
-      <c r="J9" s="16" t="n"/>
+      <c r="J9" s="22" t="n"/>
       <c r="K9" s="15" t="inlineStr">
         <is>
-          <t>Pendiente</t>
+          <t>En curso</t>
         </is>
       </c>
       <c r="L9" s="15">
@@ -7060,7 +7085,11 @@
           <t>S1-10 (#10)</t>
         </is>
       </c>
-      <c r="N9" s="15" t="inlineStr"/>
+      <c r="N9" s="15" t="inlineStr">
+        <is>
+          <t>Diego acepta la invitación el 18-oct (vencía ese día)</t>
+        </is>
+      </c>
     </row>
     <row r="10">
       <c r="A10" s="15" t="inlineStr">
@@ -7068,10 +7097,10 @@
           <t>S1-T05</t>
         </is>
       </c>
-      <c r="B10" s="16" t="n">
+      <c r="B10" s="22" t="n">
         <v>46307</v>
       </c>
-      <c r="C10" s="17">
+      <c r="C10" s="23">
         <f>B10</f>
         <v/>
       </c>
@@ -7100,13 +7129,13 @@
           <t>rag.py consultar devuelve fragmentos</t>
         </is>
       </c>
-      <c r="I10" s="18" t="n">
+      <c r="I10" s="24" t="n">
         <v>1</v>
       </c>
-      <c r="J10" s="16" t="n"/>
+      <c r="J10" s="22" t="n"/>
       <c r="K10" s="15" t="inlineStr">
         <is>
-          <t>Pendiente</t>
+          <t>Movido</t>
         </is>
       </c>
       <c r="L10" s="15">
@@ -7118,7 +7147,11 @@
           <t>S1-10 (#10)</t>
         </is>
       </c>
-      <c r="N10" s="15" t="inlineStr"/>
+      <c r="N10" s="15" t="inlineStr">
+        <is>
+          <t>Movido a la semana 19–24 oct (bloques dobles de Diego en IA_DIEGO.md)</t>
+        </is>
+      </c>
     </row>
     <row r="11">
       <c r="A11" s="15" t="inlineStr">
@@ -7126,10 +7159,10 @@
           <t>S1-T06</t>
         </is>
       </c>
-      <c r="B11" s="16" t="n">
+      <c r="B11" s="22" t="n">
         <v>46308</v>
       </c>
-      <c r="C11" s="17">
+      <c r="C11" s="23">
         <f>B11</f>
         <v/>
       </c>
@@ -7158,13 +7191,13 @@
           <t>Cada ficha con estado y página</t>
         </is>
       </c>
-      <c r="I11" s="18" t="n">
+      <c r="I11" s="24" t="n">
         <v>1</v>
       </c>
-      <c r="J11" s="16" t="n"/>
+      <c r="J11" s="22" t="n"/>
       <c r="K11" s="15" t="inlineStr">
         <is>
-          <t>Pendiente</t>
+          <t>En curso</t>
         </is>
       </c>
       <c r="L11" s="15">
@@ -7176,7 +7209,11 @@
           <t>S1-01 (#1)</t>
         </is>
       </c>
-      <c r="N11" s="15" t="inlineStr"/>
+      <c r="N11" s="15" t="inlineStr">
+        <is>
+          <t>A9 parcial (falta el PDF de Oldroyd); A10 hay que reformularla como decisión de diseño. Ver la matriz del 18-oct</t>
+        </is>
+      </c>
     </row>
     <row r="12">
       <c r="A12" s="15" t="inlineStr">
@@ -7184,10 +7221,10 @@
           <t>S1-T07</t>
         </is>
       </c>
-      <c r="B12" s="16" t="n">
+      <c r="B12" s="22" t="n">
         <v>46308</v>
       </c>
-      <c r="C12" s="17">
+      <c r="C12" s="23">
         <f>B12</f>
         <v/>
       </c>
@@ -7216,13 +7253,15 @@
           <t>Cada ficha con estado</t>
         </is>
       </c>
-      <c r="I12" s="18" t="n">
+      <c r="I12" s="24" t="n">
         <v>1</v>
       </c>
-      <c r="J12" s="16" t="n"/>
+      <c r="J12" s="22" t="n">
+        <v>46307</v>
+      </c>
       <c r="K12" s="15" t="inlineStr">
         <is>
-          <t>Pendiente</t>
+          <t>Hecho</t>
         </is>
       </c>
       <c r="L12" s="15">
@@ -7234,7 +7273,11 @@
           <t>S1-01 (#1)</t>
         </is>
       </c>
-      <c r="N12" s="15" t="inlineStr"/>
+      <c r="N12" s="15" t="inlineStr">
+        <is>
+          <t>A5 y A6 respaldadas (Manyika 2015, Cathles 2023, Samuelson 2023, McKinsey 2023). Nyqvist 2024 opcional</t>
+        </is>
+      </c>
     </row>
     <row r="13">
       <c r="A13" s="15" t="inlineStr">
@@ -7242,10 +7285,10 @@
           <t>S1-T08</t>
         </is>
       </c>
-      <c r="B13" s="16" t="n">
+      <c r="B13" s="22" t="n">
         <v>46308</v>
       </c>
-      <c r="C13" s="17">
+      <c r="C13" s="23">
         <f>B13</f>
         <v/>
       </c>
@@ -7274,13 +7317,13 @@
           <t>Cada ficha dice qué respalda</t>
         </is>
       </c>
-      <c r="I13" s="18" t="n">
+      <c r="I13" s="24" t="n">
         <v>1.5</v>
       </c>
-      <c r="J13" s="16" t="n"/>
+      <c r="J13" s="22" t="n"/>
       <c r="K13" s="15" t="inlineStr">
         <is>
-          <t>Pendiente</t>
+          <t>Movido</t>
         </is>
       </c>
       <c r="L13" s="15">
@@ -7292,7 +7335,11 @@
           <t>S1-13 (#54)</t>
         </is>
       </c>
-      <c r="N13" s="15" t="inlineStr"/>
+      <c r="N13" s="15" t="inlineStr">
+        <is>
+          <t>Movido a la semana 19–24 oct (bloques dobles de Diego en IA_DIEGO.md)</t>
+        </is>
+      </c>
     </row>
     <row r="14">
       <c r="A14" s="15" t="inlineStr">
@@ -7300,10 +7347,10 @@
           <t>S1-T09</t>
         </is>
       </c>
-      <c r="B14" s="16" t="n">
+      <c r="B14" s="22" t="n">
         <v>46308</v>
       </c>
-      <c r="C14" s="17">
+      <c r="C14" s="23">
         <f>B14</f>
         <v/>
       </c>
@@ -7332,13 +7379,13 @@
           <t>Dudas enviadas a Víctor</t>
         </is>
       </c>
-      <c r="I14" s="18" t="n">
+      <c r="I14" s="24" t="n">
         <v>0.5</v>
       </c>
-      <c r="J14" s="16" t="n"/>
+      <c r="J14" s="22" t="n"/>
       <c r="K14" s="15" t="inlineStr">
         <is>
-          <t>Pendiente</t>
+          <t>Movido</t>
         </is>
       </c>
       <c r="L14" s="15">
@@ -7350,7 +7397,11 @@
           <t>S1-10 (#10)</t>
         </is>
       </c>
-      <c r="N14" s="15" t="inlineStr"/>
+      <c r="N14" s="15" t="inlineStr">
+        <is>
+          <t>Movido a la semana 19–24 oct (bloques dobles de Diego en IA_DIEGO.md)</t>
+        </is>
+      </c>
     </row>
     <row r="15">
       <c r="A15" s="15" t="inlineStr">
@@ -7358,10 +7409,10 @@
           <t>S1-T10</t>
         </is>
       </c>
-      <c r="B15" s="16" t="n">
+      <c r="B15" s="22" t="n">
         <v>46309</v>
       </c>
-      <c r="C15" s="17">
+      <c r="C15" s="23">
         <f>B15</f>
         <v/>
       </c>
@@ -7390,13 +7441,13 @@
           <t>Notas de esta fila actualizadas</t>
         </is>
       </c>
-      <c r="I15" s="18" t="n">
+      <c r="I15" s="24" t="n">
         <v>0.25</v>
       </c>
-      <c r="J15" s="16" t="n"/>
+      <c r="J15" s="22" t="n"/>
       <c r="K15" s="15" t="inlineStr">
         <is>
-          <t>Pendiente</t>
+          <t>Movido</t>
         </is>
       </c>
       <c r="L15" s="15">
@@ -7410,7 +7461,7 @@
       </c>
       <c r="N15" s="15" t="inlineStr">
         <is>
-          <t>Plazo pedido a Torvesa: hoy</t>
+          <t>Movido: se aplica cuando Torvesa autorice (Diego consigue la información y los permisos)</t>
         </is>
       </c>
     </row>
@@ -7420,10 +7471,10 @@
           <t>S1-T11</t>
         </is>
       </c>
-      <c r="B16" s="16" t="n">
+      <c r="B16" s="22" t="n">
         <v>46309</v>
       </c>
-      <c r="C16" s="17">
+      <c r="C16" s="23">
         <f>B16</f>
         <v/>
       </c>
@@ -7452,13 +7503,15 @@
           <t>Aprobados e impresos</t>
         </is>
       </c>
-      <c r="I16" s="18" t="n">
+      <c r="I16" s="24" t="n">
         <v>0.75</v>
       </c>
-      <c r="J16" s="16" t="n"/>
+      <c r="J16" s="22" t="n">
+        <v>46313</v>
+      </c>
       <c r="K16" s="15" t="inlineStr">
         <is>
-          <t>Pendiente</t>
+          <t>Hecho</t>
         </is>
       </c>
       <c r="L16" s="15">
@@ -7470,7 +7523,11 @@
           <t>S1-04 (#4)</t>
         </is>
       </c>
-      <c r="N16" s="15" t="inlineStr"/>
+      <c r="N16" s="15" t="inlineStr">
+        <is>
+          <t>C1 v0.2 (artículos de la LOPDP) e I1 v0.2 (SUS validada en español) en 04_Instrumentos/2026-10-18_*. I2, I3, P1 y P2 siguen en v0.1</t>
+        </is>
+      </c>
     </row>
     <row r="17">
       <c r="A17" s="15" t="inlineStr">
@@ -7478,10 +7535,10 @@
           <t>S1-T12</t>
         </is>
       </c>
-      <c r="B17" s="16" t="n">
+      <c r="B17" s="22" t="n">
         <v>46309</v>
       </c>
-      <c r="C17" s="17">
+      <c r="C17" s="23">
         <f>B17</f>
         <v/>
       </c>
@@ -7510,13 +7567,15 @@
           <t>Las 47 afirmaciones tienen estado</t>
         </is>
       </c>
-      <c r="I17" s="18" t="n">
+      <c r="I17" s="24" t="n">
         <v>1</v>
       </c>
-      <c r="J17" s="16" t="n"/>
+      <c r="J17" s="22" t="n">
+        <v>46313</v>
+      </c>
       <c r="K17" s="15" t="inlineStr">
         <is>
-          <t>Pendiente</t>
+          <t>Hecho</t>
         </is>
       </c>
       <c r="L17" s="15">
@@ -7530,7 +7589,7 @@
       </c>
       <c r="N17" s="15" t="inlineStr">
         <is>
-          <t>En la noche</t>
+          <t>03_Matriz_Objetivos/2026-10-18_Matriz_Afirmaciones_v0.1.xlsx: 9 respaldadas, 7 parciales, 1 reformular, 5 de campo, 1 no se usa, 19 sin fuente</t>
         </is>
       </c>
     </row>
@@ -7540,10 +7599,10 @@
           <t>S1-T13</t>
         </is>
       </c>
-      <c r="B18" s="16" t="n">
+      <c r="B18" s="22" t="n">
         <v>46309</v>
       </c>
-      <c r="C18" s="17">
+      <c r="C18" s="23">
         <f>B18</f>
         <v/>
       </c>
@@ -7572,13 +7631,13 @@
           <t>Cada ficha dice qué respalda</t>
         </is>
       </c>
-      <c r="I18" s="18" t="n">
+      <c r="I18" s="24" t="n">
         <v>1.5</v>
       </c>
-      <c r="J18" s="16" t="n"/>
+      <c r="J18" s="22" t="n"/>
       <c r="K18" s="15" t="inlineStr">
         <is>
-          <t>Pendiente</t>
+          <t>Movido</t>
         </is>
       </c>
       <c r="L18" s="15">
@@ -7590,7 +7649,11 @@
           <t>S1-13 (#54)</t>
         </is>
       </c>
-      <c r="N18" s="15" t="inlineStr"/>
+      <c r="N18" s="15" t="inlineStr">
+        <is>
+          <t>Movido a la semana 19–24 oct (bloques dobles de Diego en IA_DIEGO.md)</t>
+        </is>
+      </c>
     </row>
     <row r="19">
       <c r="A19" s="15" t="inlineStr">
@@ -7598,10 +7661,10 @@
           <t>S1-T14</t>
         </is>
       </c>
-      <c r="B19" s="16" t="n">
+      <c r="B19" s="22" t="n">
         <v>46309</v>
       </c>
-      <c r="C19" s="17">
+      <c r="C19" s="23">
         <f>B19</f>
         <v/>
       </c>
@@ -7630,13 +7693,13 @@
           <t>Víctor lo leyó</t>
         </is>
       </c>
-      <c r="I19" s="18" t="n">
+      <c r="I19" s="24" t="n">
         <v>0.5</v>
       </c>
-      <c r="J19" s="16" t="n"/>
+      <c r="J19" s="22" t="n"/>
       <c r="K19" s="15" t="inlineStr">
         <is>
-          <t>Pendiente</t>
+          <t>Movido</t>
         </is>
       </c>
       <c r="L19" s="15">
@@ -7648,7 +7711,11 @@
           <t>S1-13 (#54)</t>
         </is>
       </c>
-      <c r="N19" s="15" t="inlineStr"/>
+      <c r="N19" s="15" t="inlineStr">
+        <is>
+          <t>Movido a la semana 19–24 oct (bloques dobles de Diego en IA_DIEGO.md)</t>
+        </is>
+      </c>
     </row>
     <row r="20">
       <c r="A20" s="15" t="inlineStr">
@@ -7656,10 +7723,10 @@
           <t>S1-T15</t>
         </is>
       </c>
-      <c r="B20" s="16" t="n">
+      <c r="B20" s="22" t="n">
         <v>46310</v>
       </c>
-      <c r="C20" s="17">
+      <c r="C20" s="23">
         <f>B20</f>
         <v/>
       </c>
@@ -7688,13 +7755,13 @@
           <t>Cada aplicación está en el registro</t>
         </is>
       </c>
-      <c r="I20" s="18" t="n">
+      <c r="I20" s="24" t="n">
         <v>2</v>
       </c>
-      <c r="J20" s="16" t="n"/>
+      <c r="J20" s="22" t="n"/>
       <c r="K20" s="15" t="inlineStr">
         <is>
-          <t>Pendiente</t>
+          <t>Movido</t>
         </is>
       </c>
       <c r="L20" s="15">
@@ -7708,7 +7775,7 @@
       </c>
       <c r="N20" s="15" t="inlineStr">
         <is>
-          <t>Si Torvesa no autorizó: adelantar la búsqueda de la ley de datos (fila del sábado)</t>
+          <t>Movido: se aplica cuando Torvesa autorice (Diego consigue la información y los permisos)</t>
         </is>
       </c>
     </row>
@@ -7718,10 +7785,10 @@
           <t>S1-T16</t>
         </is>
       </c>
-      <c r="B21" s="16" t="n">
+      <c r="B21" s="22" t="n">
         <v>46310</v>
       </c>
-      <c r="C21" s="17">
+      <c r="C21" s="23">
         <f>B21</f>
         <v/>
       </c>
@@ -7750,13 +7817,13 @@
           <t>Todas las cotizaciones observadas registradas</t>
         </is>
       </c>
-      <c r="I21" s="18" t="n">
+      <c r="I21" s="24" t="n">
         <v>2</v>
       </c>
-      <c r="J21" s="16" t="n"/>
+      <c r="J21" s="22" t="n"/>
       <c r="K21" s="15" t="inlineStr">
         <is>
-          <t>Pendiente</t>
+          <t>Movido</t>
         </is>
       </c>
       <c r="L21" s="15">
@@ -7770,7 +7837,7 @@
       </c>
       <c r="N21" s="15" t="inlineStr">
         <is>
-          <t>Si no hay autorización: adelantar la investigación de CRMs (fila del sábado)</t>
+          <t>Movido: se aplica cuando Torvesa autorice (Diego consigue la información y los permisos)</t>
         </is>
       </c>
     </row>
@@ -7780,10 +7847,10 @@
           <t>S1-T17</t>
         </is>
       </c>
-      <c r="B22" s="16" t="n">
+      <c r="B22" s="22" t="n">
         <v>46311</v>
       </c>
-      <c r="C22" s="17">
+      <c r="C22" s="23">
         <f>B22</f>
         <v/>
       </c>
@@ -7812,13 +7879,13 @@
           <t>Cada llamada con consentimiento verbal registrado</t>
         </is>
       </c>
-      <c r="I22" s="18" t="n">
+      <c r="I22" s="24" t="n">
         <v>2</v>
       </c>
-      <c r="J22" s="16" t="n"/>
+      <c r="J22" s="22" t="n"/>
       <c r="K22" s="15" t="inlineStr">
         <is>
-          <t>Pendiente</t>
+          <t>Movido</t>
         </is>
       </c>
       <c r="L22" s="15">
@@ -7830,7 +7897,11 @@
           <t>S1-08 (#8)</t>
         </is>
       </c>
-      <c r="N22" s="15" t="inlineStr"/>
+      <c r="N22" s="15" t="inlineStr">
+        <is>
+          <t>Movido: se aplica cuando Torvesa autorice (Diego consigue la información y los permisos)</t>
+        </is>
+      </c>
     </row>
     <row r="23">
       <c r="A23" s="15" t="inlineStr">
@@ -7838,10 +7909,10 @@
           <t>S1-T18</t>
         </is>
       </c>
-      <c r="B23" s="16" t="n">
+      <c r="B23" s="22" t="n">
         <v>46311</v>
       </c>
-      <c r="C23" s="17">
+      <c r="C23" s="23">
         <f>B23</f>
         <v/>
       </c>
@@ -7870,13 +7941,13 @@
           <t>≥20 solicitudes o todas las disponibles</t>
         </is>
       </c>
-      <c r="I23" s="18" t="n">
+      <c r="I23" s="24" t="n">
         <v>2</v>
       </c>
-      <c r="J23" s="16" t="n"/>
+      <c r="J23" s="22" t="n"/>
       <c r="K23" s="15" t="inlineStr">
         <is>
-          <t>Pendiente</t>
+          <t>Movido</t>
         </is>
       </c>
       <c r="L23" s="15">
@@ -7888,7 +7959,11 @@
           <t>S1-09 (#9)</t>
         </is>
       </c>
-      <c r="N23" s="15" t="inlineStr"/>
+      <c r="N23" s="15" t="inlineStr">
+        <is>
+          <t>Movido: se aplica cuando Torvesa autorice (Diego consigue la información y los permisos)</t>
+        </is>
+      </c>
     </row>
     <row r="24">
       <c r="A24" s="15" t="inlineStr">
@@ -7896,10 +7971,10 @@
           <t>S1-T19</t>
         </is>
       </c>
-      <c r="B24" s="16" t="n">
+      <c r="B24" s="22" t="n">
         <v>46312</v>
       </c>
-      <c r="C24" s="17">
+      <c r="C24" s="23">
         <f>B24</f>
         <v/>
       </c>
@@ -7928,13 +8003,15 @@
           <t>Artículos citados desde el Registro Oficial</t>
         </is>
       </c>
-      <c r="I24" s="18" t="n">
+      <c r="I24" s="24" t="n">
         <v>1.5</v>
       </c>
-      <c r="J24" s="16" t="n"/>
+      <c r="J24" s="22" t="n">
+        <v>46313</v>
+      </c>
       <c r="K24" s="15" t="inlineStr">
         <is>
-          <t>Pendiente</t>
+          <t>Hecho</t>
         </is>
       </c>
       <c r="L24" s="15">
@@ -7946,7 +8023,11 @@
           <t>S1-02 (#2)</t>
         </is>
       </c>
-      <c r="N24" s="15" t="inlineStr"/>
+      <c r="N24" s="15" t="inlineStr">
+        <is>
+          <t>LOPDP verificada en el Registro Oficial (RO 459, Quinto Suplemento, 26-may-2021) y Reglamento (Decreto 904, RO 435). Artículos en C1 v0.2</t>
+        </is>
+      </c>
     </row>
     <row r="25">
       <c r="A25" s="15" t="inlineStr">
@@ -7954,10 +8035,10 @@
           <t>S1-T20</t>
         </is>
       </c>
-      <c r="B25" s="16" t="n">
+      <c r="B25" s="22" t="n">
         <v>46312</v>
       </c>
-      <c r="C25" s="17">
+      <c r="C25" s="23">
         <f>B25</f>
         <v/>
       </c>
@@ -7986,13 +8067,15 @@
           <t>Traducción con fuente</t>
         </is>
       </c>
-      <c r="I25" s="18" t="n">
+      <c r="I25" s="24" t="n">
         <v>1</v>
       </c>
-      <c r="J25" s="16" t="n"/>
+      <c r="J25" s="22" t="n">
+        <v>46313</v>
+      </c>
       <c r="K25" s="15" t="inlineStr">
         <is>
-          <t>Pendiente</t>
+          <t>Hecho</t>
         </is>
       </c>
       <c r="L25" s="15">
@@ -8004,7 +8087,11 @@
           <t>S1-02 (#2)</t>
         </is>
       </c>
-      <c r="N25" s="15" t="inlineStr"/>
+      <c r="N25" s="15" t="inlineStr">
+        <is>
+          <t>Sevilla-Gonzalez et al. (2020), JMIR Human Factors: α = 0,812. Falta el umbral 68 (Lewis y Sauro 2018, PDF a mano)</t>
+        </is>
+      </c>
     </row>
     <row r="26">
       <c r="A26" s="15" t="inlineStr">
@@ -8012,10 +8099,10 @@
           <t>S1-T21</t>
         </is>
       </c>
-      <c r="B26" s="16" t="n">
+      <c r="B26" s="22" t="n">
         <v>46312</v>
       </c>
-      <c r="C26" s="17">
+      <c r="C26" s="23">
         <f>B26</f>
         <v/>
       </c>
@@ -8044,13 +8131,13 @@
           <t>Cada método con 2–3 fuentes</t>
         </is>
       </c>
-      <c r="I26" s="18" t="n">
+      <c r="I26" s="24" t="n">
         <v>1.5</v>
       </c>
-      <c r="J26" s="16" t="n"/>
+      <c r="J26" s="22" t="n"/>
       <c r="K26" s="15" t="inlineStr">
         <is>
-          <t>Pendiente</t>
+          <t>En curso</t>
         </is>
       </c>
       <c r="L26" s="15">
@@ -8062,7 +8149,11 @@
           <t>S1-02 (#2)</t>
         </is>
       </c>
-      <c r="N26" s="15" t="inlineStr"/>
+      <c r="N26" s="15" t="inlineStr">
+        <is>
+          <t>Verificadas: Guía Scrum 2020, Sassa 2023, Tuunanen 2024 (DSR), Dawadi 2021 (mixto), Cuadrado Torres 2023 (DT). Falta: censo (Hernández-Sampieri), DT teórico (Auernhammer 2021)</t>
+        </is>
+      </c>
     </row>
     <row r="27">
       <c r="A27" s="15" t="inlineStr">
@@ -8070,10 +8161,10 @@
           <t>S1-T22</t>
         </is>
       </c>
-      <c r="B27" s="16" t="n">
+      <c r="B27" s="22" t="n">
         <v>46312</v>
       </c>
-      <c r="C27" s="17">
+      <c r="C27" s="23">
         <f>B27</f>
         <v/>
       </c>
@@ -8102,13 +8193,13 @@
           <t>Cada ficha dice qué respalda</t>
         </is>
       </c>
-      <c r="I27" s="18" t="n">
+      <c r="I27" s="24" t="n">
         <v>1.5</v>
       </c>
-      <c r="J27" s="16" t="n"/>
+      <c r="J27" s="22" t="n"/>
       <c r="K27" s="15" t="inlineStr">
         <is>
-          <t>Pendiente</t>
+          <t>Movido</t>
         </is>
       </c>
       <c r="L27" s="15">
@@ -8120,7 +8211,11 @@
           <t>S1-14 (#55)</t>
         </is>
       </c>
-      <c r="N27" s="15" t="inlineStr"/>
+      <c r="N27" s="15" t="inlineStr">
+        <is>
+          <t>Movido a la semana 19–24 oct (bloques dobles de Diego en IA_DIEGO.md)</t>
+        </is>
+      </c>
     </row>
     <row r="28">
       <c r="A28" s="15" t="inlineStr">
@@ -8128,10 +8223,10 @@
           <t>S1-T23</t>
         </is>
       </c>
-      <c r="B28" s="16" t="n">
+      <c r="B28" s="22" t="n">
         <v>46312</v>
       </c>
-      <c r="C28" s="17">
+      <c r="C28" s="23">
         <f>B28</f>
         <v/>
       </c>
@@ -8160,13 +8255,13 @@
           <t>Cada precio con enlace oficial</t>
         </is>
       </c>
-      <c r="I28" s="18" t="n">
+      <c r="I28" s="24" t="n">
         <v>2</v>
       </c>
-      <c r="J28" s="16" t="n"/>
+      <c r="J28" s="22" t="n"/>
       <c r="K28" s="15" t="inlineStr">
         <is>
-          <t>Pendiente</t>
+          <t>Movido</t>
         </is>
       </c>
       <c r="L28" s="15">
@@ -8178,7 +8273,11 @@
           <t>S1-15 (#56)</t>
         </is>
       </c>
-      <c r="N28" s="15" t="inlineStr"/>
+      <c r="N28" s="15" t="inlineStr">
+        <is>
+          <t>Movido a la semana 19–24 oct (bloques dobles de Diego en IA_DIEGO.md)</t>
+        </is>
+      </c>
     </row>
     <row r="29">
       <c r="A29" s="15" t="inlineStr">
@@ -8186,10 +8285,10 @@
           <t>S1-T24</t>
         </is>
       </c>
-      <c r="B29" s="16" t="n">
+      <c r="B29" s="22" t="n">
         <v>46313</v>
       </c>
-      <c r="C29" s="17">
+      <c r="C29" s="23">
         <f>B29</f>
         <v/>
       </c>
@@ -8218,13 +8317,13 @@
           <t>auditoria_pii.py dice 0 hallazgos</t>
         </is>
       </c>
-      <c r="I29" s="18" t="n">
+      <c r="I29" s="24" t="n">
         <v>2</v>
       </c>
-      <c r="J29" s="16" t="n"/>
+      <c r="J29" s="22" t="n"/>
       <c r="K29" s="15" t="inlineStr">
         <is>
-          <t>Pendiente</t>
+          <t>Movido</t>
         </is>
       </c>
       <c r="L29" s="15">
@@ -8238,7 +8337,7 @@
       </c>
       <c r="N29" s="15" t="inlineStr">
         <is>
-          <t>Si no hubo campo, se mueve a la fecha nueva</t>
+          <t>Movido: se aplica cuando Torvesa autorice (Diego consigue la información y los permisos). Al día siguiente del campo</t>
         </is>
       </c>
     </row>
@@ -8248,10 +8347,10 @@
           <t>S1-T25</t>
         </is>
       </c>
-      <c r="B30" s="16" t="n">
+      <c r="B30" s="22" t="n">
         <v>46313</v>
       </c>
-      <c r="C30" s="17">
+      <c r="C30" s="23">
         <f>B30</f>
         <v/>
       </c>
@@ -8280,13 +8379,15 @@
           <t>Diego lo leyó</t>
         </is>
       </c>
-      <c r="I30" s="18" t="n">
+      <c r="I30" s="24" t="n">
         <v>0.5</v>
       </c>
-      <c r="J30" s="16" t="n"/>
+      <c r="J30" s="22" t="n">
+        <v>46313</v>
+      </c>
       <c r="K30" s="15" t="inlineStr">
         <is>
-          <t>Pendiente</t>
+          <t>Hecho</t>
         </is>
       </c>
       <c r="L30" s="15">
@@ -8298,7 +8399,11 @@
           <t>S1-01 (#1)</t>
         </is>
       </c>
-      <c r="N30" s="15" t="inlineStr"/>
+      <c r="N30" s="15" t="inlineStr">
+        <is>
+          <t>Borrador de Claude en 02_Fuentes/Problema/2026-10-18_Resumen_Problema.md; falta que Víctor lo revise</t>
+        </is>
+      </c>
     </row>
     <row r="31">
       <c r="A31" s="15" t="inlineStr">
@@ -8306,10 +8411,10 @@
           <t>S1-T26</t>
         </is>
       </c>
-      <c r="B31" s="16" t="n">
+      <c r="B31" s="22" t="n">
         <v>46313</v>
       </c>
-      <c r="C31" s="17">
+      <c r="C31" s="23">
         <f>B31</f>
         <v/>
       </c>
@@ -8338,13 +8443,13 @@
           <t>Víctor lo leyó</t>
         </is>
       </c>
-      <c r="I31" s="18" t="n">
+      <c r="I31" s="24" t="n">
         <v>0.5</v>
       </c>
-      <c r="J31" s="16" t="n"/>
+      <c r="J31" s="22" t="n"/>
       <c r="K31" s="15" t="inlineStr">
         <is>
-          <t>Pendiente</t>
+          <t>Movido</t>
         </is>
       </c>
       <c r="L31" s="15">
@@ -8356,7 +8461,11 @@
           <t>S1-15 (#56)</t>
         </is>
       </c>
-      <c r="N31" s="15" t="inlineStr"/>
+      <c r="N31" s="15" t="inlineStr">
+        <is>
+          <t>Movido a la semana 19–24 oct (bloques dobles de Diego en IA_DIEGO.md)</t>
+        </is>
+      </c>
     </row>
     <row r="32">
       <c r="A32" s="15" t="inlineStr">
@@ -8364,10 +8473,10 @@
           <t>S1-T27</t>
         </is>
       </c>
-      <c r="B32" s="16" t="n">
+      <c r="B32" s="22" t="n">
         <v>46313</v>
       </c>
-      <c r="C32" s="17">
+      <c r="C32" s="23">
         <f>B32</f>
         <v/>
       </c>
@@ -8396,13 +8505,13 @@
           <t>El informe del domingo (21:00) sale con la sección nueva</t>
         </is>
       </c>
-      <c r="I32" s="18" t="n">
+      <c r="I32" s="24" t="n">
         <v>1</v>
       </c>
-      <c r="J32" s="16" t="n"/>
+      <c r="J32" s="22" t="n"/>
       <c r="K32" s="15" t="inlineStr">
         <is>
-          <t>Pendiente</t>
+          <t>En curso</t>
         </is>
       </c>
       <c r="L32" s="15">
@@ -8414,7 +8523,11 @@
           <t>S1-16 (#57)</t>
         </is>
       </c>
-      <c r="N32" s="15" t="inlineStr"/>
+      <c r="N32" s="15" t="inlineStr">
+        <is>
+          <t>Revisión del sprint hecha por Víctor y Claude el 18-oct; falta la llamada de 20 min con Diego</t>
+        </is>
+      </c>
     </row>
   </sheetData>
   <autoFilter ref="A5:N32"/>
@@ -8540,10 +8653,10 @@
       </c>
     </row>
     <row r="5">
-      <c r="A5" s="19" t="n">
+      <c r="A5" s="25" t="n">
         <v>46307</v>
       </c>
-      <c r="B5" s="20">
+      <c r="B5" s="26">
         <f>A5</f>
         <v/>
       </c>
@@ -8569,10 +8682,10 @@
       </c>
     </row>
     <row r="6">
-      <c r="A6" s="19" t="n">
+      <c r="A6" s="25" t="n">
         <v>46308</v>
       </c>
-      <c r="B6" s="20">
+      <c r="B6" s="26">
         <f>A6</f>
         <v/>
       </c>
@@ -8598,10 +8711,10 @@
       </c>
     </row>
     <row r="7">
-      <c r="A7" s="19" t="n">
+      <c r="A7" s="25" t="n">
         <v>46309</v>
       </c>
-      <c r="B7" s="20">
+      <c r="B7" s="26">
         <f>A7</f>
         <v/>
       </c>
@@ -8627,10 +8740,10 @@
       </c>
     </row>
     <row r="8">
-      <c r="A8" s="19" t="n">
+      <c r="A8" s="25" t="n">
         <v>46310</v>
       </c>
-      <c r="B8" s="20">
+      <c r="B8" s="26">
         <f>A8</f>
         <v/>
       </c>
@@ -8656,10 +8769,10 @@
       </c>
     </row>
     <row r="9">
-      <c r="A9" s="19" t="n">
+      <c r="A9" s="25" t="n">
         <v>46311</v>
       </c>
-      <c r="B9" s="20">
+      <c r="B9" s="26">
         <f>A9</f>
         <v/>
       </c>
@@ -8685,10 +8798,10 @@
       </c>
     </row>
     <row r="10">
-      <c r="A10" s="19" t="n">
+      <c r="A10" s="25" t="n">
         <v>46312</v>
       </c>
-      <c r="B10" s="20">
+      <c r="B10" s="26">
         <f>A10</f>
         <v/>
       </c>
@@ -8714,10 +8827,10 @@
       </c>
     </row>
     <row r="11">
-      <c r="A11" s="19" t="n">
+      <c r="A11" s="25" t="n">
         <v>46313</v>
       </c>
-      <c r="B11" s="20">
+      <c r="B11" s="26">
         <f>A11</f>
         <v/>
       </c>
@@ -8743,10 +8856,10 @@
       </c>
     </row>
     <row r="12">
-      <c r="A12" s="19" t="n">
+      <c r="A12" s="25" t="n">
         <v>46314</v>
       </c>
-      <c r="B12" s="20">
+      <c r="B12" s="26">
         <f>A12</f>
         <v/>
       </c>
@@ -8772,10 +8885,10 @@
       </c>
     </row>
     <row r="13">
-      <c r="A13" s="19" t="n">
+      <c r="A13" s="25" t="n">
         <v>46315</v>
       </c>
-      <c r="B13" s="20">
+      <c r="B13" s="26">
         <f>A13</f>
         <v/>
       </c>
@@ -8801,10 +8914,10 @@
       </c>
     </row>
     <row r="14">
-      <c r="A14" s="19" t="n">
+      <c r="A14" s="25" t="n">
         <v>46316</v>
       </c>
-      <c r="B14" s="20">
+      <c r="B14" s="26">
         <f>A14</f>
         <v/>
       </c>
@@ -8830,10 +8943,10 @@
       </c>
     </row>
     <row r="15">
-      <c r="A15" s="19" t="n">
+      <c r="A15" s="25" t="n">
         <v>46317</v>
       </c>
-      <c r="B15" s="20">
+      <c r="B15" s="26">
         <f>A15</f>
         <v/>
       </c>
@@ -8859,10 +8972,10 @@
       </c>
     </row>
     <row r="16">
-      <c r="A16" s="19" t="n">
+      <c r="A16" s="25" t="n">
         <v>46318</v>
       </c>
-      <c r="B16" s="20">
+      <c r="B16" s="26">
         <f>A16</f>
         <v/>
       </c>
@@ -8888,10 +9001,10 @@
       </c>
     </row>
     <row r="17">
-      <c r="A17" s="19" t="n">
+      <c r="A17" s="25" t="n">
         <v>46319</v>
       </c>
-      <c r="B17" s="20">
+      <c r="B17" s="26">
         <f>A17</f>
         <v/>
       </c>
@@ -8917,10 +9030,10 @@
       </c>
     </row>
     <row r="18">
-      <c r="A18" s="19" t="n">
+      <c r="A18" s="25" t="n">
         <v>46320</v>
       </c>
-      <c r="B18" s="20">
+      <c r="B18" s="26">
         <f>A18</f>
         <v/>
       </c>
@@ -8946,10 +9059,10 @@
       </c>
     </row>
     <row r="19">
-      <c r="A19" s="19" t="n">
+      <c r="A19" s="25" t="n">
         <v>46321</v>
       </c>
-      <c r="B19" s="20">
+      <c r="B19" s="26">
         <f>A19</f>
         <v/>
       </c>
@@ -8975,10 +9088,10 @@
       </c>
     </row>
     <row r="20">
-      <c r="A20" s="19" t="n">
+      <c r="A20" s="25" t="n">
         <v>46322</v>
       </c>
-      <c r="B20" s="20">
+      <c r="B20" s="26">
         <f>A20</f>
         <v/>
       </c>
@@ -9004,10 +9117,10 @@
       </c>
     </row>
     <row r="21">
-      <c r="A21" s="19" t="n">
+      <c r="A21" s="25" t="n">
         <v>46323</v>
       </c>
-      <c r="B21" s="20">
+      <c r="B21" s="26">
         <f>A21</f>
         <v/>
       </c>
@@ -9033,10 +9146,10 @@
       </c>
     </row>
     <row r="22">
-      <c r="A22" s="19" t="n">
+      <c r="A22" s="25" t="n">
         <v>46324</v>
       </c>
-      <c r="B22" s="20">
+      <c r="B22" s="26">
         <f>A22</f>
         <v/>
       </c>
@@ -9062,10 +9175,10 @@
       </c>
     </row>
     <row r="23">
-      <c r="A23" s="19" t="n">
+      <c r="A23" s="25" t="n">
         <v>46325</v>
       </c>
-      <c r="B23" s="20">
+      <c r="B23" s="26">
         <f>A23</f>
         <v/>
       </c>
@@ -9091,10 +9204,10 @@
       </c>
     </row>
     <row r="24">
-      <c r="A24" s="19" t="n">
+      <c r="A24" s="25" t="n">
         <v>46326</v>
       </c>
-      <c r="B24" s="20">
+      <c r="B24" s="26">
         <f>A24</f>
         <v/>
       </c>
@@ -9120,10 +9233,10 @@
       </c>
     </row>
     <row r="25">
-      <c r="A25" s="19" t="n">
+      <c r="A25" s="25" t="n">
         <v>46327</v>
       </c>
-      <c r="B25" s="20">
+      <c r="B25" s="26">
         <f>A25</f>
         <v/>
       </c>
@@ -9149,10 +9262,10 @@
       </c>
     </row>
     <row r="26">
-      <c r="A26" s="19" t="n">
+      <c r="A26" s="25" t="n">
         <v>46328</v>
       </c>
-      <c r="B26" s="20">
+      <c r="B26" s="26">
         <f>A26</f>
         <v/>
       </c>
@@ -9178,10 +9291,10 @@
       </c>
     </row>
     <row r="27">
-      <c r="A27" s="19" t="n">
+      <c r="A27" s="25" t="n">
         <v>46329</v>
       </c>
-      <c r="B27" s="20">
+      <c r="B27" s="26">
         <f>A27</f>
         <v/>
       </c>
@@ -9207,10 +9320,10 @@
       </c>
     </row>
     <row r="28">
-      <c r="A28" s="19" t="n">
+      <c r="A28" s="25" t="n">
         <v>46330</v>
       </c>
-      <c r="B28" s="20">
+      <c r="B28" s="26">
         <f>A28</f>
         <v/>
       </c>
@@ -9236,10 +9349,10 @@
       </c>
     </row>
     <row r="29">
-      <c r="A29" s="19" t="n">
+      <c r="A29" s="25" t="n">
         <v>46331</v>
       </c>
-      <c r="B29" s="20">
+      <c r="B29" s="26">
         <f>A29</f>
         <v/>
       </c>
@@ -9265,10 +9378,10 @@
       </c>
     </row>
     <row r="30">
-      <c r="A30" s="19" t="n">
+      <c r="A30" s="25" t="n">
         <v>46332</v>
       </c>
-      <c r="B30" s="20">
+      <c r="B30" s="26">
         <f>A30</f>
         <v/>
       </c>
@@ -9294,10 +9407,10 @@
       </c>
     </row>
     <row r="31">
-      <c r="A31" s="19" t="n">
+      <c r="A31" s="25" t="n">
         <v>46333</v>
       </c>
-      <c r="B31" s="20">
+      <c r="B31" s="26">
         <f>A31</f>
         <v/>
       </c>
@@ -9323,10 +9436,10 @@
       </c>
     </row>
     <row r="32">
-      <c r="A32" s="19" t="n">
+      <c r="A32" s="25" t="n">
         <v>46334</v>
       </c>
-      <c r="B32" s="20">
+      <c r="B32" s="26">
         <f>A32</f>
         <v/>
       </c>
@@ -9352,10 +9465,10 @@
       </c>
     </row>
     <row r="33">
-      <c r="A33" s="19" t="n">
+      <c r="A33" s="25" t="n">
         <v>46335</v>
       </c>
-      <c r="B33" s="20">
+      <c r="B33" s="26">
         <f>A33</f>
         <v/>
       </c>
@@ -9381,10 +9494,10 @@
       </c>
     </row>
     <row r="34">
-      <c r="A34" s="19" t="n">
+      <c r="A34" s="25" t="n">
         <v>46336</v>
       </c>
-      <c r="B34" s="20">
+      <c r="B34" s="26">
         <f>A34</f>
         <v/>
       </c>
@@ -9410,10 +9523,10 @@
       </c>
     </row>
     <row r="35">
-      <c r="A35" s="19" t="n">
+      <c r="A35" s="25" t="n">
         <v>46337</v>
       </c>
-      <c r="B35" s="20">
+      <c r="B35" s="26">
         <f>A35</f>
         <v/>
       </c>
@@ -9439,10 +9552,10 @@
       </c>
     </row>
     <row r="36">
-      <c r="A36" s="19" t="n">
+      <c r="A36" s="25" t="n">
         <v>46338</v>
       </c>
-      <c r="B36" s="20">
+      <c r="B36" s="26">
         <f>A36</f>
         <v/>
       </c>
@@ -9468,10 +9581,10 @@
       </c>
     </row>
     <row r="37">
-      <c r="A37" s="19" t="n">
+      <c r="A37" s="25" t="n">
         <v>46339</v>
       </c>
-      <c r="B37" s="20">
+      <c r="B37" s="26">
         <f>A37</f>
         <v/>
       </c>
@@ -9497,10 +9610,10 @@
       </c>
     </row>
     <row r="38">
-      <c r="A38" s="19" t="n">
+      <c r="A38" s="25" t="n">
         <v>46340</v>
       </c>
-      <c r="B38" s="20">
+      <c r="B38" s="26">
         <f>A38</f>
         <v/>
       </c>
@@ -9526,10 +9639,10 @@
       </c>
     </row>
     <row r="39">
-      <c r="A39" s="19" t="n">
+      <c r="A39" s="25" t="n">
         <v>46341</v>
       </c>
-      <c r="B39" s="20">
+      <c r="B39" s="26">
         <f>A39</f>
         <v/>
       </c>
@@ -9555,10 +9668,10 @@
       </c>
     </row>
     <row r="40">
-      <c r="A40" s="19" t="n">
+      <c r="A40" s="25" t="n">
         <v>46342</v>
       </c>
-      <c r="B40" s="20">
+      <c r="B40" s="26">
         <f>A40</f>
         <v/>
       </c>
@@ -9584,10 +9697,10 @@
       </c>
     </row>
     <row r="41">
-      <c r="A41" s="19" t="n">
+      <c r="A41" s="25" t="n">
         <v>46343</v>
       </c>
-      <c r="B41" s="20">
+      <c r="B41" s="26">
         <f>A41</f>
         <v/>
       </c>
@@ -9613,10 +9726,10 @@
       </c>
     </row>
     <row r="42">
-      <c r="A42" s="19" t="n">
+      <c r="A42" s="25" t="n">
         <v>46344</v>
       </c>
-      <c r="B42" s="20">
+      <c r="B42" s="26">
         <f>A42</f>
         <v/>
       </c>
@@ -9642,10 +9755,10 @@
       </c>
     </row>
     <row r="43">
-      <c r="A43" s="19" t="n">
+      <c r="A43" s="25" t="n">
         <v>46345</v>
       </c>
-      <c r="B43" s="20">
+      <c r="B43" s="26">
         <f>A43</f>
         <v/>
       </c>
@@ -9671,10 +9784,10 @@
       </c>
     </row>
     <row r="44">
-      <c r="A44" s="19" t="n">
+      <c r="A44" s="25" t="n">
         <v>46346</v>
       </c>
-      <c r="B44" s="20">
+      <c r="B44" s="26">
         <f>A44</f>
         <v/>
       </c>
@@ -9700,10 +9813,10 @@
       </c>
     </row>
     <row r="45">
-      <c r="A45" s="19" t="n">
+      <c r="A45" s="25" t="n">
         <v>46347</v>
       </c>
-      <c r="B45" s="20">
+      <c r="B45" s="26">
         <f>A45</f>
         <v/>
       </c>
@@ -9729,10 +9842,10 @@
       </c>
     </row>
     <row r="46">
-      <c r="A46" s="19" t="n">
+      <c r="A46" s="25" t="n">
         <v>46348</v>
       </c>
-      <c r="B46" s="20">
+      <c r="B46" s="26">
         <f>A46</f>
         <v/>
       </c>
@@ -9758,10 +9871,10 @@
       </c>
     </row>
     <row r="47">
-      <c r="A47" s="19" t="n">
+      <c r="A47" s="25" t="n">
         <v>46349</v>
       </c>
-      <c r="B47" s="20">
+      <c r="B47" s="26">
         <f>A47</f>
         <v/>
       </c>
@@ -9787,10 +9900,10 @@
       </c>
     </row>
     <row r="48">
-      <c r="A48" s="19" t="n">
+      <c r="A48" s="25" t="n">
         <v>46350</v>
       </c>
-      <c r="B48" s="20">
+      <c r="B48" s="26">
         <f>A48</f>
         <v/>
       </c>
@@ -9816,10 +9929,10 @@
       </c>
     </row>
     <row r="49">
-      <c r="A49" s="19" t="n">
+      <c r="A49" s="25" t="n">
         <v>46351</v>
       </c>
-      <c r="B49" s="20">
+      <c r="B49" s="26">
         <f>A49</f>
         <v/>
       </c>
@@ -9845,10 +9958,10 @@
       </c>
     </row>
     <row r="50">
-      <c r="A50" s="19" t="n">
+      <c r="A50" s="25" t="n">
         <v>46352</v>
       </c>
-      <c r="B50" s="20">
+      <c r="B50" s="26">
         <f>A50</f>
         <v/>
       </c>
@@ -9874,10 +9987,10 @@
       </c>
     </row>
     <row r="51">
-      <c r="A51" s="19" t="n">
+      <c r="A51" s="25" t="n">
         <v>46353</v>
       </c>
-      <c r="B51" s="20">
+      <c r="B51" s="26">
         <f>A51</f>
         <v/>
       </c>
@@ -9903,10 +10016,10 @@
       </c>
     </row>
     <row r="52">
-      <c r="A52" s="19" t="n">
+      <c r="A52" s="25" t="n">
         <v>46354</v>
       </c>
-      <c r="B52" s="20">
+      <c r="B52" s="26">
         <f>A52</f>
         <v/>
       </c>
@@ -9932,10 +10045,10 @@
       </c>
     </row>
     <row r="53">
-      <c r="A53" s="19" t="n">
+      <c r="A53" s="25" t="n">
         <v>46355</v>
       </c>
-      <c r="B53" s="20">
+      <c r="B53" s="26">
         <f>A53</f>
         <v/>
       </c>
@@ -9961,10 +10074,10 @@
       </c>
     </row>
     <row r="54">
-      <c r="A54" s="19" t="n">
+      <c r="A54" s="25" t="n">
         <v>46356</v>
       </c>
-      <c r="B54" s="20">
+      <c r="B54" s="26">
         <f>A54</f>
         <v/>
       </c>
@@ -9990,10 +10103,10 @@
       </c>
     </row>
     <row r="55">
-      <c r="A55" s="19" t="n">
+      <c r="A55" s="25" t="n">
         <v>46357</v>
       </c>
-      <c r="B55" s="20">
+      <c r="B55" s="26">
         <f>A55</f>
         <v/>
       </c>
@@ -10019,10 +10132,10 @@
       </c>
     </row>
     <row r="56">
-      <c r="A56" s="19" t="n">
+      <c r="A56" s="25" t="n">
         <v>46358</v>
       </c>
-      <c r="B56" s="20">
+      <c r="B56" s="26">
         <f>A56</f>
         <v/>
       </c>
@@ -10048,10 +10161,10 @@
       </c>
     </row>
     <row r="57">
-      <c r="A57" s="19" t="n">
+      <c r="A57" s="25" t="n">
         <v>46359</v>
       </c>
-      <c r="B57" s="20">
+      <c r="B57" s="26">
         <f>A57</f>
         <v/>
       </c>
@@ -10077,10 +10190,10 @@
       </c>
     </row>
     <row r="58">
-      <c r="A58" s="19" t="n">
+      <c r="A58" s="25" t="n">
         <v>46360</v>
       </c>
-      <c r="B58" s="20">
+      <c r="B58" s="26">
         <f>A58</f>
         <v/>
       </c>
@@ -10106,10 +10219,10 @@
       </c>
     </row>
     <row r="59">
-      <c r="A59" s="19" t="n">
+      <c r="A59" s="25" t="n">
         <v>46361</v>
       </c>
-      <c r="B59" s="20">
+      <c r="B59" s="26">
         <f>A59</f>
         <v/>
       </c>
@@ -10135,10 +10248,10 @@
       </c>
     </row>
     <row r="60">
-      <c r="A60" s="19" t="n">
+      <c r="A60" s="25" t="n">
         <v>46362</v>
       </c>
-      <c r="B60" s="20">
+      <c r="B60" s="26">
         <f>A60</f>
         <v/>
       </c>
@@ -10164,10 +10277,10 @@
       </c>
     </row>
     <row r="61">
-      <c r="A61" s="19" t="n">
+      <c r="A61" s="25" t="n">
         <v>46363</v>
       </c>
-      <c r="B61" s="20">
+      <c r="B61" s="26">
         <f>A61</f>
         <v/>
       </c>
@@ -10193,10 +10306,10 @@
       </c>
     </row>
     <row r="62">
-      <c r="A62" s="19" t="n">
+      <c r="A62" s="25" t="n">
         <v>46364</v>
       </c>
-      <c r="B62" s="20">
+      <c r="B62" s="26">
         <f>A62</f>
         <v/>
       </c>
@@ -10222,10 +10335,10 @@
       </c>
     </row>
     <row r="63">
-      <c r="A63" s="19" t="n">
+      <c r="A63" s="25" t="n">
         <v>46365</v>
       </c>
-      <c r="B63" s="20">
+      <c r="B63" s="26">
         <f>A63</f>
         <v/>
       </c>
@@ -10251,10 +10364,10 @@
       </c>
     </row>
     <row r="64">
-      <c r="A64" s="19" t="n">
+      <c r="A64" s="25" t="n">
         <v>46366</v>
       </c>
-      <c r="B64" s="20">
+      <c r="B64" s="26">
         <f>A64</f>
         <v/>
       </c>
@@ -10280,10 +10393,10 @@
       </c>
     </row>
     <row r="65">
-      <c r="A65" s="19" t="n">
+      <c r="A65" s="25" t="n">
         <v>46367</v>
       </c>
-      <c r="B65" s="20">
+      <c r="B65" s="26">
         <f>A65</f>
         <v/>
       </c>
@@ -10309,10 +10422,10 @@
       </c>
     </row>
     <row r="66">
-      <c r="A66" s="19" t="n">
+      <c r="A66" s="25" t="n">
         <v>46368</v>
       </c>
-      <c r="B66" s="20">
+      <c r="B66" s="26">
         <f>A66</f>
         <v/>
       </c>
@@ -10338,10 +10451,10 @@
       </c>
     </row>
     <row r="67">
-      <c r="A67" s="19" t="n">
+      <c r="A67" s="25" t="n">
         <v>46369</v>
       </c>
-      <c r="B67" s="20">
+      <c r="B67" s="26">
         <f>A67</f>
         <v/>
       </c>
@@ -10367,10 +10480,10 @@
       </c>
     </row>
     <row r="68">
-      <c r="A68" s="19" t="n">
+      <c r="A68" s="25" t="n">
         <v>46370</v>
       </c>
-      <c r="B68" s="20">
+      <c r="B68" s="26">
         <f>A68</f>
         <v/>
       </c>
@@ -10396,10 +10509,10 @@
       </c>
     </row>
     <row r="69">
-      <c r="A69" s="19" t="n">
+      <c r="A69" s="25" t="n">
         <v>46371</v>
       </c>
-      <c r="B69" s="20">
+      <c r="B69" s="26">
         <f>A69</f>
         <v/>
       </c>
@@ -10425,10 +10538,10 @@
       </c>
     </row>
     <row r="70">
-      <c r="A70" s="19" t="n">
+      <c r="A70" s="25" t="n">
         <v>46372</v>
       </c>
-      <c r="B70" s="20">
+      <c r="B70" s="26">
         <f>A70</f>
         <v/>
       </c>
@@ -10454,10 +10567,10 @@
       </c>
     </row>
     <row r="71">
-      <c r="A71" s="19" t="n">
+      <c r="A71" s="25" t="n">
         <v>46373</v>
       </c>
-      <c r="B71" s="20">
+      <c r="B71" s="26">
         <f>A71</f>
         <v/>
       </c>
@@ -10483,10 +10596,10 @@
       </c>
     </row>
     <row r="72">
-      <c r="A72" s="19" t="n">
+      <c r="A72" s="25" t="n">
         <v>46374</v>
       </c>
-      <c r="B72" s="20">
+      <c r="B72" s="26">
         <f>A72</f>
         <v/>
       </c>
@@ -10512,10 +10625,10 @@
       </c>
     </row>
     <row r="73">
-      <c r="A73" s="19" t="n">
+      <c r="A73" s="25" t="n">
         <v>46375</v>
       </c>
-      <c r="B73" s="20">
+      <c r="B73" s="26">
         <f>A73</f>
         <v/>
       </c>
@@ -10541,10 +10654,10 @@
       </c>
     </row>
     <row r="74">
-      <c r="A74" s="19" t="n">
+      <c r="A74" s="25" t="n">
         <v>46376</v>
       </c>
-      <c r="B74" s="20">
+      <c r="B74" s="26">
         <f>A74</f>
         <v/>
       </c>
@@ -10570,10 +10683,10 @@
       </c>
     </row>
     <row r="75">
-      <c r="A75" s="19" t="n">
+      <c r="A75" s="25" t="n">
         <v>46377</v>
       </c>
-      <c r="B75" s="20">
+      <c r="B75" s="26">
         <f>A75</f>
         <v/>
       </c>
@@ -10599,10 +10712,10 @@
       </c>
     </row>
     <row r="76">
-      <c r="A76" s="19" t="n">
+      <c r="A76" s="25" t="n">
         <v>46378</v>
       </c>
-      <c r="B76" s="20">
+      <c r="B76" s="26">
         <f>A76</f>
         <v/>
       </c>
@@ -10628,10 +10741,10 @@
       </c>
     </row>
     <row r="77">
-      <c r="A77" s="19" t="n">
+      <c r="A77" s="25" t="n">
         <v>46379</v>
       </c>
-      <c r="B77" s="20">
+      <c r="B77" s="26">
         <f>A77</f>
         <v/>
       </c>
@@ -10657,10 +10770,10 @@
       </c>
     </row>
     <row r="78">
-      <c r="A78" s="19" t="n">
+      <c r="A78" s="25" t="n">
         <v>46380</v>
       </c>
-      <c r="B78" s="20">
+      <c r="B78" s="26">
         <f>A78</f>
         <v/>
       </c>
@@ -10686,10 +10799,10 @@
       </c>
     </row>
     <row r="79">
-      <c r="A79" s="19" t="n">
+      <c r="A79" s="25" t="n">
         <v>46381</v>
       </c>
-      <c r="B79" s="20">
+      <c r="B79" s="26">
         <f>A79</f>
         <v/>
       </c>
@@ -10715,10 +10828,10 @@
       </c>
     </row>
     <row r="80">
-      <c r="A80" s="19" t="n">
+      <c r="A80" s="25" t="n">
         <v>46382</v>
       </c>
-      <c r="B80" s="20">
+      <c r="B80" s="26">
         <f>A80</f>
         <v/>
       </c>
@@ -10744,10 +10857,10 @@
       </c>
     </row>
     <row r="81">
-      <c r="A81" s="19" t="n">
+      <c r="A81" s="25" t="n">
         <v>46383</v>
       </c>
-      <c r="B81" s="20">
+      <c r="B81" s="26">
         <f>A81</f>
         <v/>
       </c>
@@ -10773,10 +10886,10 @@
       </c>
     </row>
     <row r="82">
-      <c r="A82" s="19" t="n">
+      <c r="A82" s="25" t="n">
         <v>46384</v>
       </c>
-      <c r="B82" s="20">
+      <c r="B82" s="26">
         <f>A82</f>
         <v/>
       </c>
@@ -10802,10 +10915,10 @@
       </c>
     </row>
     <row r="83">
-      <c r="A83" s="19" t="n">
+      <c r="A83" s="25" t="n">
         <v>46385</v>
       </c>
-      <c r="B83" s="20">
+      <c r="B83" s="26">
         <f>A83</f>
         <v/>
       </c>
@@ -10831,10 +10944,10 @@
       </c>
     </row>
     <row r="84">
-      <c r="A84" s="19" t="n">
+      <c r="A84" s="25" t="n">
         <v>46386</v>
       </c>
-      <c r="B84" s="20">
+      <c r="B84" s="26">
         <f>A84</f>
         <v/>
       </c>
@@ -10860,10 +10973,10 @@
       </c>
     </row>
     <row r="85">
-      <c r="A85" s="19" t="n">
+      <c r="A85" s="25" t="n">
         <v>46387</v>
       </c>
-      <c r="B85" s="20">
+      <c r="B85" s="26">
         <f>A85</f>
         <v/>
       </c>
@@ -10889,10 +11002,10 @@
       </c>
     </row>
     <row r="86">
-      <c r="A86" s="19" t="n">
+      <c r="A86" s="25" t="n">
         <v>46388</v>
       </c>
-      <c r="B86" s="20">
+      <c r="B86" s="26">
         <f>A86</f>
         <v/>
       </c>
@@ -10918,10 +11031,10 @@
       </c>
     </row>
     <row r="87">
-      <c r="A87" s="19" t="n">
+      <c r="A87" s="25" t="n">
         <v>46389</v>
       </c>
-      <c r="B87" s="20">
+      <c r="B87" s="26">
         <f>A87</f>
         <v/>
       </c>
@@ -10947,10 +11060,10 @@
       </c>
     </row>
     <row r="88">
-      <c r="A88" s="19" t="n">
+      <c r="A88" s="25" t="n">
         <v>46390</v>
       </c>
-      <c r="B88" s="20">
+      <c r="B88" s="26">
         <f>A88</f>
         <v/>
       </c>
@@ -10976,10 +11089,10 @@
       </c>
     </row>
     <row r="89">
-      <c r="A89" s="19" t="n">
+      <c r="A89" s="25" t="n">
         <v>46391</v>
       </c>
-      <c r="B89" s="20">
+      <c r="B89" s="26">
         <f>A89</f>
         <v/>
       </c>
@@ -11005,10 +11118,10 @@
       </c>
     </row>
     <row r="90">
-      <c r="A90" s="19" t="n">
+      <c r="A90" s="25" t="n">
         <v>46392</v>
       </c>
-      <c r="B90" s="20">
+      <c r="B90" s="26">
         <f>A90</f>
         <v/>
       </c>
@@ -11034,10 +11147,10 @@
       </c>
     </row>
     <row r="91">
-      <c r="A91" s="19" t="n">
+      <c r="A91" s="25" t="n">
         <v>46393</v>
       </c>
-      <c r="B91" s="20">
+      <c r="B91" s="26">
         <f>A91</f>
         <v/>
       </c>
@@ -11063,10 +11176,10 @@
       </c>
     </row>
     <row r="92">
-      <c r="A92" s="19" t="n">
+      <c r="A92" s="25" t="n">
         <v>46394</v>
       </c>
-      <c r="B92" s="20">
+      <c r="B92" s="26">
         <f>A92</f>
         <v/>
       </c>
@@ -11092,10 +11205,10 @@
       </c>
     </row>
     <row r="93">
-      <c r="A93" s="19" t="n">
+      <c r="A93" s="25" t="n">
         <v>46395</v>
       </c>
-      <c r="B93" s="20">
+      <c r="B93" s="26">
         <f>A93</f>
         <v/>
       </c>
@@ -11121,10 +11234,10 @@
       </c>
     </row>
     <row r="94">
-      <c r="A94" s="19" t="n">
+      <c r="A94" s="25" t="n">
         <v>46396</v>
       </c>
-      <c r="B94" s="20">
+      <c r="B94" s="26">
         <f>A94</f>
         <v/>
       </c>
@@ -11150,10 +11263,10 @@
       </c>
     </row>
     <row r="95">
-      <c r="A95" s="19" t="n">
+      <c r="A95" s="25" t="n">
         <v>46397</v>
       </c>
-      <c r="B95" s="20">
+      <c r="B95" s="26">
         <f>A95</f>
         <v/>
       </c>
@@ -11179,10 +11292,10 @@
       </c>
     </row>
     <row r="96">
-      <c r="A96" s="19" t="n">
+      <c r="A96" s="25" t="n">
         <v>46398</v>
       </c>
-      <c r="B96" s="20">
+      <c r="B96" s="26">
         <f>A96</f>
         <v/>
       </c>
@@ -11208,10 +11321,10 @@
       </c>
     </row>
     <row r="97">
-      <c r="A97" s="19" t="n">
+      <c r="A97" s="25" t="n">
         <v>46399</v>
       </c>
-      <c r="B97" s="20">
+      <c r="B97" s="26">
         <f>A97</f>
         <v/>
       </c>
@@ -11237,10 +11350,10 @@
       </c>
     </row>
     <row r="98">
-      <c r="A98" s="19" t="n">
+      <c r="A98" s="25" t="n">
         <v>46400</v>
       </c>
-      <c r="B98" s="20">
+      <c r="B98" s="26">
         <f>A98</f>
         <v/>
       </c>
@@ -11266,10 +11379,10 @@
       </c>
     </row>
     <row r="99">
-      <c r="A99" s="19" t="n">
+      <c r="A99" s="25" t="n">
         <v>46401</v>
       </c>
-      <c r="B99" s="20">
+      <c r="B99" s="26">
         <f>A99</f>
         <v/>
       </c>
@@ -11295,10 +11408,10 @@
       </c>
     </row>
     <row r="100">
-      <c r="A100" s="19" t="n">
+      <c r="A100" s="25" t="n">
         <v>46402</v>
       </c>
-      <c r="B100" s="20">
+      <c r="B100" s="26">
         <f>A100</f>
         <v/>
       </c>
@@ -11324,10 +11437,10 @@
       </c>
     </row>
     <row r="101">
-      <c r="A101" s="19" t="n">
+      <c r="A101" s="25" t="n">
         <v>46403</v>
       </c>
-      <c r="B101" s="20">
+      <c r="B101" s="26">
         <f>A101</f>
         <v/>
       </c>
@@ -11353,10 +11466,10 @@
       </c>
     </row>
     <row r="102">
-      <c r="A102" s="19" t="n">
+      <c r="A102" s="25" t="n">
         <v>46404</v>
       </c>
-      <c r="B102" s="20">
+      <c r="B102" s="26">
         <f>A102</f>
         <v/>
       </c>
@@ -11382,10 +11495,10 @@
       </c>
     </row>
     <row r="103">
-      <c r="A103" s="19" t="n">
+      <c r="A103" s="25" t="n">
         <v>46405</v>
       </c>
-      <c r="B103" s="20">
+      <c r="B103" s="26">
         <f>A103</f>
         <v/>
       </c>
@@ -11411,10 +11524,10 @@
       </c>
     </row>
     <row r="104">
-      <c r="A104" s="19" t="n">
+      <c r="A104" s="25" t="n">
         <v>46406</v>
       </c>
-      <c r="B104" s="20">
+      <c r="B104" s="26">
         <f>A104</f>
         <v/>
       </c>
@@ -11440,10 +11553,10 @@
       </c>
     </row>
     <row r="105">
-      <c r="A105" s="19" t="n">
+      <c r="A105" s="25" t="n">
         <v>46407</v>
       </c>
-      <c r="B105" s="20">
+      <c r="B105" s="26">
         <f>A105</f>
         <v/>
       </c>
@@ -11469,10 +11582,10 @@
       </c>
     </row>
     <row r="106">
-      <c r="A106" s="19" t="n">
+      <c r="A106" s="25" t="n">
         <v>46408</v>
       </c>
-      <c r="B106" s="20">
+      <c r="B106" s="26">
         <f>A106</f>
         <v/>
       </c>
@@ -11498,10 +11611,10 @@
       </c>
     </row>
     <row r="107">
-      <c r="A107" s="19" t="n">
+      <c r="A107" s="25" t="n">
         <v>46409</v>
       </c>
-      <c r="B107" s="20">
+      <c r="B107" s="26">
         <f>A107</f>
         <v/>
       </c>
@@ -11527,10 +11640,10 @@
       </c>
     </row>
     <row r="108">
-      <c r="A108" s="19" t="n">
+      <c r="A108" s="25" t="n">
         <v>46410</v>
       </c>
-      <c r="B108" s="20">
+      <c r="B108" s="26">
         <f>A108</f>
         <v/>
       </c>
@@ -11556,10 +11669,10 @@
       </c>
     </row>
     <row r="109">
-      <c r="A109" s="19" t="n">
+      <c r="A109" s="25" t="n">
         <v>46411</v>
       </c>
-      <c r="B109" s="20">
+      <c r="B109" s="26">
         <f>A109</f>
         <v/>
       </c>
@@ -11585,10 +11698,10 @@
       </c>
     </row>
     <row r="110">
-      <c r="A110" s="19" t="n">
+      <c r="A110" s="25" t="n">
         <v>46412</v>
       </c>
-      <c r="B110" s="20">
+      <c r="B110" s="26">
         <f>A110</f>
         <v/>
       </c>
@@ -11614,10 +11727,10 @@
       </c>
     </row>
     <row r="111">
-      <c r="A111" s="19" t="n">
+      <c r="A111" s="25" t="n">
         <v>46413</v>
       </c>
-      <c r="B111" s="20">
+      <c r="B111" s="26">
         <f>A111</f>
         <v/>
       </c>
@@ -11643,10 +11756,10 @@
       </c>
     </row>
     <row r="112">
-      <c r="A112" s="19" t="n">
+      <c r="A112" s="25" t="n">
         <v>46414</v>
       </c>
-      <c r="B112" s="20">
+      <c r="B112" s="26">
         <f>A112</f>
         <v/>
       </c>
@@ -11672,10 +11785,10 @@
       </c>
     </row>
     <row r="113">
-      <c r="A113" s="19" t="n">
+      <c r="A113" s="25" t="n">
         <v>46415</v>
       </c>
-      <c r="B113" s="20">
+      <c r="B113" s="26">
         <f>A113</f>
         <v/>
       </c>
@@ -11701,10 +11814,10 @@
       </c>
     </row>
     <row r="114">
-      <c r="A114" s="19" t="n">
+      <c r="A114" s="25" t="n">
         <v>46416</v>
       </c>
-      <c r="B114" s="20">
+      <c r="B114" s="26">
         <f>A114</f>
         <v/>
       </c>
@@ -11730,10 +11843,10 @@
       </c>
     </row>
     <row r="115">
-      <c r="A115" s="19" t="n">
+      <c r="A115" s="25" t="n">
         <v>46417</v>
       </c>
-      <c r="B115" s="20">
+      <c r="B115" s="26">
         <f>A115</f>
         <v/>
       </c>
@@ -11759,10 +11872,10 @@
       </c>
     </row>
     <row r="116">
-      <c r="A116" s="19" t="n">
+      <c r="A116" s="25" t="n">
         <v>46418</v>
       </c>
-      <c r="B116" s="20">
+      <c r="B116" s="26">
         <f>A116</f>
         <v/>
       </c>
@@ -11788,10 +11901,10 @@
       </c>
     </row>
     <row r="117">
-      <c r="A117" s="19" t="n">
+      <c r="A117" s="25" t="n">
         <v>46419</v>
       </c>
-      <c r="B117" s="20">
+      <c r="B117" s="26">
         <f>A117</f>
         <v/>
       </c>
@@ -11817,10 +11930,10 @@
       </c>
     </row>
     <row r="118">
-      <c r="A118" s="19" t="n">
+      <c r="A118" s="25" t="n">
         <v>46420</v>
       </c>
-      <c r="B118" s="20">
+      <c r="B118" s="26">
         <f>A118</f>
         <v/>
       </c>
@@ -11846,10 +11959,10 @@
       </c>
     </row>
     <row r="119">
-      <c r="A119" s="19" t="n">
+      <c r="A119" s="25" t="n">
         <v>46421</v>
       </c>
-      <c r="B119" s="20">
+      <c r="B119" s="26">
         <f>A119</f>
         <v/>
       </c>
@@ -11875,10 +11988,10 @@
       </c>
     </row>
     <row r="120">
-      <c r="A120" s="19" t="n">
+      <c r="A120" s="25" t="n">
         <v>46422</v>
       </c>
-      <c r="B120" s="20">
+      <c r="B120" s="26">
         <f>A120</f>
         <v/>
       </c>
@@ -11904,10 +12017,10 @@
       </c>
     </row>
     <row r="121">
-      <c r="A121" s="19" t="n">
+      <c r="A121" s="25" t="n">
         <v>46423</v>
       </c>
-      <c r="B121" s="20">
+      <c r="B121" s="26">
         <f>A121</f>
         <v/>
       </c>
@@ -11933,10 +12046,10 @@
       </c>
     </row>
     <row r="122">
-      <c r="A122" s="19" t="n">
+      <c r="A122" s="25" t="n">
         <v>46424</v>
       </c>
-      <c r="B122" s="20">
+      <c r="B122" s="26">
         <f>A122</f>
         <v/>
       </c>
@@ -11962,10 +12075,10 @@
       </c>
     </row>
     <row r="123">
-      <c r="A123" s="19" t="n">
+      <c r="A123" s="25" t="n">
         <v>46425</v>
       </c>
-      <c r="B123" s="20">
+      <c r="B123" s="26">
         <f>A123</f>
         <v/>
       </c>
@@ -11991,10 +12104,10 @@
       </c>
     </row>
     <row r="124">
-      <c r="A124" s="19" t="n">
+      <c r="A124" s="25" t="n">
         <v>46426</v>
       </c>
-      <c r="B124" s="20">
+      <c r="B124" s="26">
         <f>A124</f>
         <v/>
       </c>
@@ -12020,10 +12133,10 @@
       </c>
     </row>
     <row r="125">
-      <c r="A125" s="19" t="n">
+      <c r="A125" s="25" t="n">
         <v>46427</v>
       </c>
-      <c r="B125" s="20">
+      <c r="B125" s="26">
         <f>A125</f>
         <v/>
       </c>
@@ -12049,10 +12162,10 @@
       </c>
     </row>
     <row r="126">
-      <c r="A126" s="19" t="n">
+      <c r="A126" s="25" t="n">
         <v>46428</v>
       </c>
-      <c r="B126" s="20">
+      <c r="B126" s="26">
         <f>A126</f>
         <v/>
       </c>
@@ -12078,10 +12191,10 @@
       </c>
     </row>
     <row r="127">
-      <c r="A127" s="19" t="n">
+      <c r="A127" s="25" t="n">
         <v>46429</v>
       </c>
-      <c r="B127" s="20">
+      <c r="B127" s="26">
         <f>A127</f>
         <v/>
       </c>
@@ -12107,10 +12220,10 @@
       </c>
     </row>
     <row r="128">
-      <c r="A128" s="19" t="n">
+      <c r="A128" s="25" t="n">
         <v>46430</v>
       </c>
-      <c r="B128" s="20">
+      <c r="B128" s="26">
         <f>A128</f>
         <v/>
       </c>
@@ -12235,6 +12348,7 @@
         <v/>
       </c>
     </row>
+    <row r="4"/>
     <row r="5" ht="30" customHeight="1">
       <c r="A5" s="14" t="inlineStr">
         <is>
@@ -12313,10 +12427,10 @@
           <t>S2-T01</t>
         </is>
       </c>
-      <c r="B6" s="16" t="n">
+      <c r="B6" s="22" t="n">
         <v>46314</v>
       </c>
-      <c r="C6" s="17">
+      <c r="C6" s="23">
         <f>B6</f>
         <v/>
       </c>
@@ -12345,10 +12459,10 @@
           <t>Cada cifra enlazada a su ficha verificada</t>
         </is>
       </c>
-      <c r="I6" s="18" t="n">
+      <c r="I6" s="24" t="n">
         <v>2</v>
       </c>
-      <c r="J6" s="16" t="n"/>
+      <c r="J6" s="22" t="n"/>
       <c r="K6" s="15" t="inlineStr">
         <is>
           <t>Pendiente</t>
@@ -12363,7 +12477,11 @@
           <t>S2-01 (#13)</t>
         </is>
       </c>
-      <c r="N6" s="15" t="inlineStr"/>
+      <c r="N6" s="15" t="inlineStr">
+        <is>
+          <t>Bloque doble con: bajar a mano los PDF de la matriz (Oldroyd, Pollitt, Galan, Nyqvist, Lewis y Sauro, Auernhammer) → Claude los verifica</t>
+        </is>
+      </c>
     </row>
     <row r="7">
       <c r="A7" s="15" t="inlineStr">
@@ -12371,10 +12489,10 @@
           <t>S2-T02</t>
         </is>
       </c>
-      <c r="B7" s="16" t="n">
+      <c r="B7" s="22" t="n">
         <v>46314</v>
       </c>
-      <c r="C7" s="17">
+      <c r="C7" s="23">
         <f>B7</f>
         <v/>
       </c>
@@ -12403,10 +12521,10 @@
           <t>Tablas de M1–M4 y M6</t>
         </is>
       </c>
-      <c r="I7" s="18" t="n">
+      <c r="I7" s="24" t="n">
         <v>2</v>
       </c>
-      <c r="J7" s="16" t="n"/>
+      <c r="J7" s="22" t="n"/>
       <c r="K7" s="15" t="inlineStr">
         <is>
           <t>Pendiente</t>
@@ -12423,7 +12541,7 @@
       </c>
       <c r="N7" s="15" t="inlineStr">
         <is>
-          <t>Si no hubo campo: analizar la muestra documental disponible</t>
+          <t>Depende del campo. Mientras tanto Diego sigue con lo movido del S1 (IA_DIEGO.md)</t>
         </is>
       </c>
     </row>
@@ -12433,10 +12551,10 @@
           <t>S2-T03</t>
         </is>
       </c>
-      <c r="B8" s="16" t="n">
+      <c r="B8" s="22" t="n">
         <v>46315</v>
       </c>
-      <c r="C8" s="17">
+      <c r="C8" s="23">
         <f>B8</f>
         <v/>
       </c>
@@ -12465,10 +12583,10 @@
           <t>Capítulo completo, revisado una vez</t>
         </is>
       </c>
-      <c r="I8" s="18" t="n">
+      <c r="I8" s="24" t="n">
         <v>2</v>
       </c>
-      <c r="J8" s="16" t="n"/>
+      <c r="J8" s="22" t="n"/>
       <c r="K8" s="15" t="inlineStr">
         <is>
           <t>Pendiente</t>
@@ -12483,7 +12601,11 @@
           <t>S2-01 (#13)</t>
         </is>
       </c>
-      <c r="N8" s="15" t="inlineStr"/>
+      <c r="N8" s="15" t="inlineStr">
+        <is>
+          <t>Bloque doble con: fuentes de CRM A21–A27 (Claude busca y verifica, Víctor revisa)</t>
+        </is>
+      </c>
     </row>
     <row r="9">
       <c r="A9" s="15" t="inlineStr">
@@ -12491,10 +12613,10 @@
           <t>S2-T04</t>
         </is>
       </c>
-      <c r="B9" s="16" t="n">
+      <c r="B9" s="22" t="n">
         <v>46315</v>
       </c>
-      <c r="C9" s="17">
+      <c r="C9" s="23">
         <f>B9</f>
         <v/>
       </c>
@@ -12523,10 +12645,10 @@
           <t>Víctor entiende cada número</t>
         </is>
       </c>
-      <c r="I9" s="18" t="n">
+      <c r="I9" s="24" t="n">
         <v>2</v>
       </c>
-      <c r="J9" s="16" t="n"/>
+      <c r="J9" s="22" t="n"/>
       <c r="K9" s="15" t="inlineStr">
         <is>
           <t>Pendiente</t>
@@ -12541,7 +12663,11 @@
           <t>S2-04 (#16)</t>
         </is>
       </c>
-      <c r="N9" s="15" t="inlineStr"/>
+      <c r="N9" s="15" t="inlineStr">
+        <is>
+          <t>Depende del campo</t>
+        </is>
+      </c>
     </row>
     <row r="10">
       <c r="A10" s="15" t="inlineStr">
@@ -12549,10 +12675,10 @@
           <t>S2-T05</t>
         </is>
       </c>
-      <c r="B10" s="16" t="n">
+      <c r="B10" s="22" t="n">
         <v>46316</v>
       </c>
-      <c r="C10" s="17">
+      <c r="C10" s="23">
         <f>B10</f>
         <v/>
       </c>
@@ -12581,10 +12707,10 @@
           <t>Solo fuentes verificadas</t>
         </is>
       </c>
-      <c r="I10" s="18" t="n">
+      <c r="I10" s="24" t="n">
         <v>2</v>
       </c>
-      <c r="J10" s="16" t="n"/>
+      <c r="J10" s="22" t="n"/>
       <c r="K10" s="15" t="inlineStr">
         <is>
           <t>Pendiente</t>
@@ -12599,7 +12725,11 @@
           <t>S2-02 (#14)</t>
         </is>
       </c>
-      <c r="N10" s="15" t="inlineStr"/>
+      <c r="N10" s="15" t="inlineStr">
+        <is>
+          <t>Bloque doble con: censo y métodos A40–A41 (biblioteca UPS: Hernández-Sampieri y Mendoza, 2018)</t>
+        </is>
+      </c>
     </row>
     <row r="11">
       <c r="A11" s="15" t="inlineStr">
@@ -12607,10 +12737,10 @@
           <t>S2-T06</t>
         </is>
       </c>
-      <c r="B11" s="16" t="n">
+      <c r="B11" s="22" t="n">
         <v>46316</v>
       </c>
-      <c r="C11" s="17">
+      <c r="C11" s="23">
         <f>B11</f>
         <v/>
       </c>
@@ -12639,10 +12769,10 @@
           <t>Cada paso tiene quién lo hace</t>
         </is>
       </c>
-      <c r="I11" s="18" t="n">
+      <c r="I11" s="24" t="n">
         <v>2</v>
       </c>
-      <c r="J11" s="16" t="n"/>
+      <c r="J11" s="22" t="n"/>
       <c r="K11" s="15" t="inlineStr">
         <is>
           <t>Pendiente</t>
@@ -12657,7 +12787,11 @@
           <t>S2-05 (#17)</t>
         </is>
       </c>
-      <c r="N11" s="15" t="inlineStr"/>
+      <c r="N11" s="15" t="inlineStr">
+        <is>
+          <t>Empezar el borrador con los documentos que hay (informe final del 22-jul y diagnóstico) y completarlo con las entrevistas cuando haya campo</t>
+        </is>
+      </c>
     </row>
     <row r="12">
       <c r="A12" s="15" t="inlineStr">
@@ -12665,10 +12799,10 @@
           <t>S2-T07</t>
         </is>
       </c>
-      <c r="B12" s="16" t="n">
+      <c r="B12" s="22" t="n">
         <v>46317</v>
       </c>
-      <c r="C12" s="17">
+      <c r="C12" s="23">
         <f>B12</f>
         <v/>
       </c>
@@ -12697,10 +12831,10 @@
           <t>Capítulo completo</t>
         </is>
       </c>
-      <c r="I12" s="18" t="n">
+      <c r="I12" s="24" t="n">
         <v>2</v>
       </c>
-      <c r="J12" s="16" t="n"/>
+      <c r="J12" s="22" t="n"/>
       <c r="K12" s="15" t="inlineStr">
         <is>
           <t>Pendiente</t>
@@ -12715,7 +12849,11 @@
           <t>S2-02 (#14)</t>
         </is>
       </c>
-      <c r="N12" s="15" t="inlineStr"/>
+      <c r="N12" s="15" t="inlineStr">
+        <is>
+          <t>Bloque doble con: A44 (Ley de Comercio Electrónico) y A30 (blockchain)</t>
+        </is>
+      </c>
     </row>
     <row r="13">
       <c r="A13" s="15" t="inlineStr">
@@ -12723,10 +12861,10 @@
           <t>S2-T08</t>
         </is>
       </c>
-      <c r="B13" s="16" t="n">
+      <c r="B13" s="22" t="n">
         <v>46317</v>
       </c>
-      <c r="C13" s="17">
+      <c r="C13" s="23">
         <f>B13</f>
         <v/>
       </c>
@@ -12755,10 +12893,10 @@
           <t>Validado contra las entrevistas</t>
         </is>
       </c>
-      <c r="I13" s="18" t="n">
+      <c r="I13" s="24" t="n">
         <v>2</v>
       </c>
-      <c r="J13" s="16" t="n"/>
+      <c r="J13" s="22" t="n"/>
       <c r="K13" s="15" t="inlineStr">
         <is>
           <t>Pendiente</t>
@@ -12781,10 +12919,10 @@
           <t>S2-T09</t>
         </is>
       </c>
-      <c r="B14" s="16" t="n">
+      <c r="B14" s="22" t="n">
         <v>46318</v>
       </c>
-      <c r="C14" s="17">
+      <c r="C14" s="23">
         <f>B14</f>
         <v/>
       </c>
@@ -12813,10 +12951,10 @@
           <t>Cada ficha con estado</t>
         </is>
       </c>
-      <c r="I14" s="18" t="n">
+      <c r="I14" s="24" t="n">
         <v>1</v>
       </c>
-      <c r="J14" s="16" t="n"/>
+      <c r="J14" s="22" t="n"/>
       <c r="K14" s="15" t="inlineStr">
         <is>
           <t>Pendiente</t>
@@ -12839,10 +12977,10 @@
           <t>S2-T10</t>
         </is>
       </c>
-      <c r="B15" s="16" t="n">
+      <c r="B15" s="22" t="n">
         <v>46318</v>
       </c>
-      <c r="C15" s="17">
+      <c r="C15" s="23">
         <f>B15</f>
         <v/>
       </c>
@@ -12871,10 +13009,10 @@
           <t>9 bloques completos</t>
         </is>
       </c>
-      <c r="I15" s="18" t="n">
+      <c r="I15" s="24" t="n">
         <v>1</v>
       </c>
-      <c r="J15" s="16" t="n"/>
+      <c r="J15" s="22" t="n"/>
       <c r="K15" s="15" t="inlineStr">
         <is>
           <t>Pendiente</t>
@@ -12897,10 +13035,10 @@
           <t>S2-T11</t>
         </is>
       </c>
-      <c r="B16" s="16" t="n">
+      <c r="B16" s="22" t="n">
         <v>46318</v>
       </c>
-      <c r="C16" s="17">
+      <c r="C16" s="23">
         <f>B16</f>
         <v/>
       </c>
@@ -12929,10 +13067,10 @@
           <t>≥3 opciones por componente</t>
         </is>
       </c>
-      <c r="I16" s="18" t="n">
+      <c r="I16" s="24" t="n">
         <v>2</v>
       </c>
-      <c r="J16" s="16" t="n"/>
+      <c r="J16" s="22" t="n"/>
       <c r="K16" s="15" t="inlineStr">
         <is>
           <t>Pendiente</t>
@@ -12955,10 +13093,10 @@
           <t>S2-T12</t>
         </is>
       </c>
-      <c r="B17" s="16" t="n">
+      <c r="B17" s="22" t="n">
         <v>46319</v>
       </c>
-      <c r="C17" s="17">
+      <c r="C17" s="23">
         <f>B17</f>
         <v/>
       </c>
@@ -12987,10 +13125,10 @@
           <t>Coherente con D1 y D2</t>
         </is>
       </c>
-      <c r="I17" s="18" t="n">
+      <c r="I17" s="24" t="n">
         <v>3</v>
       </c>
-      <c r="J17" s="16" t="n"/>
+      <c r="J17" s="22" t="n"/>
       <c r="K17" s="15" t="inlineStr">
         <is>
           <t>Pendiente</t>
@@ -13013,10 +13151,10 @@
           <t>S2-T13</t>
         </is>
       </c>
-      <c r="B18" s="16" t="n">
+      <c r="B18" s="22" t="n">
         <v>46319</v>
       </c>
-      <c r="C18" s="17">
+      <c r="C18" s="23">
         <f>B18</f>
         <v/>
       </c>
@@ -13045,10 +13183,10 @@
           <t>Diego lo leyó</t>
         </is>
       </c>
-      <c r="I18" s="18" t="n">
+      <c r="I18" s="24" t="n">
         <v>0.5</v>
       </c>
-      <c r="J18" s="16" t="n"/>
+      <c r="J18" s="22" t="n"/>
       <c r="K18" s="15" t="inlineStr">
         <is>
           <t>Pendiente</t>
@@ -13071,10 +13209,10 @@
           <t>S2-T14</t>
         </is>
       </c>
-      <c r="B19" s="16" t="n">
+      <c r="B19" s="22" t="n">
         <v>46319</v>
       </c>
-      <c r="C19" s="17">
+      <c r="C19" s="23">
         <f>B19</f>
         <v/>
       </c>
@@ -13103,10 +13241,10 @@
           <t>Cada precio con fuente</t>
         </is>
       </c>
-      <c r="I19" s="18" t="n">
+      <c r="I19" s="24" t="n">
         <v>2.5</v>
       </c>
-      <c r="J19" s="16" t="n"/>
+      <c r="J19" s="22" t="n"/>
       <c r="K19" s="15" t="inlineStr">
         <is>
           <t>Pendiente</t>
@@ -13129,10 +13267,10 @@
           <t>S2-T15</t>
         </is>
       </c>
-      <c r="B20" s="16" t="n">
+      <c r="B20" s="22" t="n">
         <v>46319</v>
       </c>
-      <c r="C20" s="17">
+      <c r="C20" s="23">
         <f>B20</f>
         <v/>
       </c>
@@ -13161,10 +13299,10 @@
           <t>Víctor lo leyó</t>
         </is>
       </c>
-      <c r="I20" s="18" t="n">
+      <c r="I20" s="24" t="n">
         <v>0.5</v>
       </c>
-      <c r="J20" s="16" t="n"/>
+      <c r="J20" s="22" t="n"/>
       <c r="K20" s="15" t="inlineStr">
         <is>
           <t>Pendiente</t>
@@ -13187,10 +13325,10 @@
           <t>S2-T16</t>
         </is>
       </c>
-      <c r="B21" s="16" t="n">
+      <c r="B21" s="22" t="n">
         <v>46320</v>
       </c>
-      <c r="C21" s="17">
+      <c r="C21" s="23">
         <f>B21</f>
         <v/>
       </c>
@@ -13219,10 +13357,10 @@
           <t>Capítulo completo</t>
         </is>
       </c>
-      <c r="I21" s="18" t="n">
+      <c r="I21" s="24" t="n">
         <v>2</v>
       </c>
-      <c r="J21" s="16" t="n"/>
+      <c r="J21" s="22" t="n"/>
       <c r="K21" s="15" t="inlineStr">
         <is>
           <t>Pendiente</t>
@@ -13245,10 +13383,10 @@
           <t>S2-T17</t>
         </is>
       </c>
-      <c r="B22" s="16" t="n">
+      <c r="B22" s="22" t="n">
         <v>46320</v>
       </c>
-      <c r="C22" s="17">
+      <c r="C22" s="23">
         <f>B22</f>
         <v/>
       </c>
@@ -13277,10 +13415,10 @@
           <t>Gráficas legibles con título</t>
         </is>
       </c>
-      <c r="I22" s="18" t="n">
+      <c r="I22" s="24" t="n">
         <v>2</v>
       </c>
-      <c r="J22" s="16" t="n"/>
+      <c r="J22" s="22" t="n"/>
       <c r="K22" s="15" t="inlineStr">
         <is>
           <t>Pendiente</t>
@@ -13303,10 +13441,10 @@
           <t>S2-T18</t>
         </is>
       </c>
-      <c r="B23" s="16" t="n">
+      <c r="B23" s="22" t="n">
         <v>46320</v>
       </c>
-      <c r="C23" s="17">
+      <c r="C23" s="23">
         <f>B23</f>
         <v/>
       </c>
@@ -13335,10 +13473,10 @@
           <t>El informe del domingo (21:00) sale con la sección nueva</t>
         </is>
       </c>
-      <c r="I23" s="18" t="n">
+      <c r="I23" s="24" t="n">
         <v>1</v>
       </c>
-      <c r="J23" s="16" t="n"/>
+      <c r="J23" s="22" t="n"/>
       <c r="K23" s="15" t="inlineStr">
         <is>
           <t>Pendiente</t>
@@ -13541,10 +13679,10 @@
           <t>S3-T01</t>
         </is>
       </c>
-      <c r="B6" s="16" t="n">
+      <c r="B6" s="22" t="n">
         <v>46321</v>
       </c>
-      <c r="C6" s="17">
+      <c r="C6" s="23">
         <f>B6</f>
         <v/>
       </c>
@@ -13573,10 +13711,10 @@
           <t>Máx. 12 diapositivas</t>
         </is>
       </c>
-      <c r="I6" s="18" t="n">
+      <c r="I6" s="24" t="n">
         <v>2</v>
       </c>
-      <c r="J6" s="16" t="n"/>
+      <c r="J6" s="22" t="n"/>
       <c r="K6" s="15" t="inlineStr">
         <is>
           <t>Pendiente</t>
@@ -13599,10 +13737,10 @@
           <t>S3-T02</t>
         </is>
       </c>
-      <c r="B7" s="16" t="n">
+      <c r="B7" s="22" t="n">
         <v>46321</v>
       </c>
-      <c r="C7" s="17">
+      <c r="C7" s="23">
         <f>B7</f>
         <v/>
       </c>
@@ -13631,10 +13769,10 @@
           <t>Se leen bien proyectadas</t>
         </is>
       </c>
-      <c r="I7" s="18" t="n">
+      <c r="I7" s="24" t="n">
         <v>2</v>
       </c>
-      <c r="J7" s="16" t="n"/>
+      <c r="J7" s="22" t="n"/>
       <c r="K7" s="15" t="inlineStr">
         <is>
           <t>Pendiente</t>
@@ -13657,10 +13795,10 @@
           <t>S3-T03</t>
         </is>
       </c>
-      <c r="B8" s="16" t="n">
+      <c r="B8" s="22" t="n">
         <v>46322</v>
       </c>
-      <c r="C8" s="17">
+      <c r="C8" s="23">
         <f>B8</f>
         <v/>
       </c>
@@ -13689,10 +13827,10 @@
           <t>Dura ≤15 min</t>
         </is>
       </c>
-      <c r="I8" s="18" t="n">
+      <c r="I8" s="24" t="n">
         <v>1</v>
       </c>
-      <c r="J8" s="16" t="n"/>
+      <c r="J8" s="22" t="n"/>
       <c r="K8" s="15" t="inlineStr">
         <is>
           <t>Pendiente</t>
@@ -13715,10 +13853,10 @@
           <t>S3-T04</t>
         </is>
       </c>
-      <c r="B9" s="16" t="n">
+      <c r="B9" s="22" t="n">
         <v>46322</v>
       </c>
-      <c r="C9" s="17">
+      <c r="C9" s="23">
         <f>B9</f>
         <v/>
       </c>
@@ -13747,10 +13885,10 @@
           <t>Sin datos de CRISFE</t>
         </is>
       </c>
-      <c r="I9" s="18" t="n">
+      <c r="I9" s="24" t="n">
         <v>1</v>
       </c>
-      <c r="J9" s="16" t="n"/>
+      <c r="J9" s="22" t="n"/>
       <c r="K9" s="15" t="inlineStr">
         <is>
           <t>Pendiente</t>
@@ -13773,10 +13911,10 @@
           <t>S3-T05</t>
         </is>
       </c>
-      <c r="B10" s="16" t="n">
+      <c r="B10" s="22" t="n">
         <v>46323</v>
       </c>
-      <c r="C10" s="17">
+      <c r="C10" s="23">
         <f>B10</f>
         <v/>
       </c>
@@ -13805,10 +13943,10 @@
           <t>Reunión realizada</t>
         </is>
       </c>
-      <c r="I10" s="18" t="n">
+      <c r="I10" s="24" t="n">
         <v>1.5</v>
       </c>
-      <c r="J10" s="16" t="n"/>
+      <c r="J10" s="22" t="n"/>
       <c r="K10" s="15" t="inlineStr">
         <is>
           <t>Pendiente</t>
@@ -13835,10 +13973,10 @@
           <t>S3-T06</t>
         </is>
       </c>
-      <c r="B11" s="16" t="n">
+      <c r="B11" s="22" t="n">
         <v>46323</v>
       </c>
-      <c r="C11" s="17">
+      <c r="C11" s="23">
         <f>B11</f>
         <v/>
       </c>
@@ -13867,10 +14005,10 @@
           <t>Cada observación con responsable y plazo</t>
         </is>
       </c>
-      <c r="I11" s="18" t="n">
+      <c r="I11" s="24" t="n">
         <v>0.5</v>
       </c>
-      <c r="J11" s="16" t="n"/>
+      <c r="J11" s="22" t="n"/>
       <c r="K11" s="15" t="inlineStr">
         <is>
           <t>Pendiente</t>
@@ -13893,10 +14031,10 @@
           <t>S3-T07</t>
         </is>
       </c>
-      <c r="B12" s="16" t="n">
+      <c r="B12" s="22" t="n">
         <v>46324</v>
       </c>
-      <c r="C12" s="17">
+      <c r="C12" s="23">
         <f>B12</f>
         <v/>
       </c>
@@ -13925,10 +14063,10 @@
           <t>Observaciones marcadas como cerradas</t>
         </is>
       </c>
-      <c r="I12" s="18" t="n">
+      <c r="I12" s="24" t="n">
         <v>2</v>
       </c>
-      <c r="J12" s="16" t="n"/>
+      <c r="J12" s="22" t="n"/>
       <c r="K12" s="15" t="inlineStr">
         <is>
           <t>Pendiente</t>
@@ -13951,10 +14089,10 @@
           <t>S3-T08</t>
         </is>
       </c>
-      <c r="B13" s="16" t="n">
+      <c r="B13" s="22" t="n">
         <v>46324</v>
       </c>
-      <c r="C13" s="17">
+      <c r="C13" s="23">
         <f>B13</f>
         <v/>
       </c>
@@ -13983,10 +14121,10 @@
           <t>Observaciones cerradas</t>
         </is>
       </c>
-      <c r="I13" s="18" t="n">
+      <c r="I13" s="24" t="n">
         <v>2</v>
       </c>
-      <c r="J13" s="16" t="n"/>
+      <c r="J13" s="22" t="n"/>
       <c r="K13" s="15" t="inlineStr">
         <is>
           <t>Pendiente</t>
@@ -14009,10 +14147,10 @@
           <t>S3-T09</t>
         </is>
       </c>
-      <c r="B14" s="16" t="n">
+      <c r="B14" s="22" t="n">
         <v>46325</v>
       </c>
-      <c r="C14" s="17">
+      <c r="C14" s="23">
         <f>B14</f>
         <v/>
       </c>
@@ -14041,10 +14179,10 @@
           <t>Documento completo, sin datos</t>
         </is>
       </c>
-      <c r="I14" s="18" t="n">
+      <c r="I14" s="24" t="n">
         <v>1.5</v>
       </c>
-      <c r="J14" s="16" t="n"/>
+      <c r="J14" s="22" t="n"/>
       <c r="K14" s="15" t="inlineStr">
         <is>
           <t>Pendiente</t>
@@ -14067,10 +14205,10 @@
           <t>S3-T10</t>
         </is>
       </c>
-      <c r="B15" s="16" t="n">
+      <c r="B15" s="22" t="n">
         <v>46325</v>
       </c>
-      <c r="C15" s="17">
+      <c r="C15" s="23">
         <f>B15</f>
         <v/>
       </c>
@@ -14099,10 +14237,10 @@
           <t>Preguntas enviadas</t>
         </is>
       </c>
-      <c r="I15" s="18" t="n">
+      <c r="I15" s="24" t="n">
         <v>1</v>
       </c>
-      <c r="J15" s="16" t="n"/>
+      <c r="J15" s="22" t="n"/>
       <c r="K15" s="15" t="inlineStr">
         <is>
           <t>Pendiente</t>
@@ -14125,10 +14263,10 @@
           <t>S3-T11</t>
         </is>
       </c>
-      <c r="B16" s="16" t="n">
+      <c r="B16" s="22" t="n">
         <v>46326</v>
       </c>
-      <c r="C16" s="17">
+      <c r="C16" s="23">
         <f>B16</f>
         <v/>
       </c>
@@ -14157,10 +14295,10 @@
           <t>Todas las observaciones cerradas</t>
         </is>
       </c>
-      <c r="I16" s="18" t="n">
+      <c r="I16" s="24" t="n">
         <v>3</v>
       </c>
-      <c r="J16" s="16" t="n"/>
+      <c r="J16" s="22" t="n"/>
       <c r="K16" s="15" t="inlineStr">
         <is>
           <t>Pendiente</t>
@@ -14183,10 +14321,10 @@
           <t>S3-T12</t>
         </is>
       </c>
-      <c r="B17" s="16" t="n">
+      <c r="B17" s="22" t="n">
         <v>46326</v>
       </c>
-      <c r="C17" s="17">
+      <c r="C17" s="23">
         <f>B17</f>
         <v/>
       </c>
@@ -14215,10 +14353,10 @@
           <t>Lista para el lunes</t>
         </is>
       </c>
-      <c r="I17" s="18" t="n">
+      <c r="I17" s="24" t="n">
         <v>2</v>
       </c>
-      <c r="J17" s="16" t="n"/>
+      <c r="J17" s="22" t="n"/>
       <c r="K17" s="15" t="inlineStr">
         <is>
           <t>Pendiente</t>
@@ -14241,10 +14379,10 @@
           <t>S3-T13</t>
         </is>
       </c>
-      <c r="B18" s="16" t="n">
+      <c r="B18" s="22" t="n">
         <v>46327</v>
       </c>
-      <c r="C18" s="17">
+      <c r="C18" s="23">
         <f>B18</f>
         <v/>
       </c>
@@ -14273,10 +14411,10 @@
           <t>Lista de funciones anotada</t>
         </is>
       </c>
-      <c r="I18" s="18" t="n">
+      <c r="I18" s="24" t="n">
         <v>1</v>
       </c>
-      <c r="J18" s="16" t="n"/>
+      <c r="J18" s="22" t="n"/>
       <c r="K18" s="15" t="inlineStr">
         <is>
           <t>Pendiente</t>
@@ -14299,10 +14437,10 @@
           <t>S3-T14</t>
         </is>
       </c>
-      <c r="B19" s="16" t="n">
+      <c r="B19" s="22" t="n">
         <v>46327</v>
       </c>
-      <c r="C19" s="17">
+      <c r="C19" s="23">
         <f>B19</f>
         <v/>
       </c>
@@ -14331,10 +14469,10 @@
           <t>El informe del domingo (21:00) sale con la sección nueva</t>
         </is>
       </c>
-      <c r="I19" s="18" t="n">
+      <c r="I19" s="24" t="n">
         <v>1</v>
       </c>
-      <c r="J19" s="16" t="n"/>
+      <c r="J19" s="22" t="n"/>
       <c r="K19" s="15" t="inlineStr">
         <is>
           <t>Pendiente</t>
@@ -14537,10 +14675,10 @@
           <t>S4-T01</t>
         </is>
       </c>
-      <c r="B6" s="16" t="n">
+      <c r="B6" s="22" t="n">
         <v>46328</v>
       </c>
-      <c r="C6" s="17">
+      <c r="C6" s="23">
         <f>B6</f>
         <v/>
       </c>
@@ -14569,10 +14707,10 @@
           <t>Cada paso con disparador y responsable</t>
         </is>
       </c>
-      <c r="I6" s="18" t="n">
+      <c r="I6" s="24" t="n">
         <v>2</v>
       </c>
-      <c r="J6" s="16" t="n"/>
+      <c r="J6" s="22" t="n"/>
       <c r="K6" s="15" t="inlineStr">
         <is>
           <t>Pendiente</t>
@@ -14595,10 +14733,10 @@
           <t>S4-T02</t>
         </is>
       </c>
-      <c r="B7" s="16" t="n">
+      <c r="B7" s="22" t="n">
         <v>46328</v>
       </c>
-      <c r="C7" s="17">
+      <c r="C7" s="23">
         <f>B7</f>
         <v/>
       </c>
@@ -14627,10 +14765,10 @@
           <t>Cada requisito con su origen</t>
         </is>
       </c>
-      <c r="I7" s="18" t="n">
+      <c r="I7" s="24" t="n">
         <v>2</v>
       </c>
-      <c r="J7" s="16" t="n"/>
+      <c r="J7" s="22" t="n"/>
       <c r="K7" s="15" t="inlineStr">
         <is>
           <t>Pendiente</t>
@@ -14653,10 +14791,10 @@
           <t>S4-T03</t>
         </is>
       </c>
-      <c r="B8" s="16" t="n">
+      <c r="B8" s="22" t="n">
         <v>46329</v>
       </c>
-      <c r="C8" s="17">
+      <c r="C8" s="23">
         <f>B8</f>
         <v/>
       </c>
@@ -14685,10 +14823,10 @@
           <t>Cubre los pasos 3–4</t>
         </is>
       </c>
-      <c r="I8" s="18" t="n">
+      <c r="I8" s="24" t="n">
         <v>2</v>
       </c>
-      <c r="J8" s="16" t="n"/>
+      <c r="J8" s="22" t="n"/>
       <c r="K8" s="15" t="inlineStr">
         <is>
           <t>Pendiente</t>
@@ -14711,10 +14849,10 @@
           <t>S4-T04</t>
         </is>
       </c>
-      <c r="B9" s="16" t="n">
+      <c r="B9" s="22" t="n">
         <v>46329</v>
       </c>
-      <c r="C9" s="17">
+      <c r="C9" s="23">
         <f>B9</f>
         <v/>
       </c>
@@ -14743,10 +14881,10 @@
           <t>Requisitos completos</t>
         </is>
       </c>
-      <c r="I9" s="18" t="n">
+      <c r="I9" s="24" t="n">
         <v>2</v>
       </c>
-      <c r="J9" s="16" t="n"/>
+      <c r="J9" s="22" t="n"/>
       <c r="K9" s="15" t="inlineStr">
         <is>
           <t>Pendiente</t>
@@ -14769,10 +14907,10 @@
           <t>S4-T05</t>
         </is>
       </c>
-      <c r="B10" s="16" t="n">
+      <c r="B10" s="22" t="n">
         <v>46330</v>
       </c>
-      <c r="C10" s="17">
+      <c r="C10" s="23">
         <f>B10</f>
         <v/>
       </c>
@@ -14801,10 +14939,10 @@
           <t>Cubre los 6 pasos</t>
         </is>
       </c>
-      <c r="I10" s="18" t="n">
+      <c r="I10" s="24" t="n">
         <v>2</v>
       </c>
-      <c r="J10" s="16" t="n"/>
+      <c r="J10" s="22" t="n"/>
       <c r="K10" s="15" t="inlineStr">
         <is>
           <t>Pendiente</t>
@@ -14827,10 +14965,10 @@
           <t>S4-T06</t>
         </is>
       </c>
-      <c r="B11" s="16" t="n">
+      <c r="B11" s="22" t="n">
         <v>46330</v>
       </c>
-      <c r="C11" s="17">
+      <c r="C11" s="23">
         <f>B11</f>
         <v/>
       </c>
@@ -14859,10 +14997,10 @@
           <t>Cada requisito ligado a un flujo</t>
         </is>
       </c>
-      <c r="I11" s="18" t="n">
+      <c r="I11" s="24" t="n">
         <v>1.5</v>
       </c>
-      <c r="J11" s="16" t="n"/>
+      <c r="J11" s="22" t="n"/>
       <c r="K11" s="15" t="inlineStr">
         <is>
           <t>Pendiente</t>
@@ -14885,10 +15023,10 @@
           <t>S4-T07</t>
         </is>
       </c>
-      <c r="B12" s="16" t="n">
+      <c r="B12" s="22" t="n">
         <v>46331</v>
       </c>
-      <c r="C12" s="17">
+      <c r="C12" s="23">
         <f>B12</f>
         <v/>
       </c>
@@ -14917,10 +15055,10 @@
           <t>Estructura creada</t>
         </is>
       </c>
-      <c r="I12" s="18" t="n">
+      <c r="I12" s="24" t="n">
         <v>2</v>
       </c>
-      <c r="J12" s="16" t="n"/>
+      <c r="J12" s="22" t="n"/>
       <c r="K12" s="15" t="inlineStr">
         <is>
           <t>Pendiente</t>
@@ -14943,10 +15081,10 @@
           <t>S4-T08</t>
         </is>
       </c>
-      <c r="B13" s="16" t="n">
+      <c r="B13" s="22" t="n">
         <v>46331</v>
       </c>
-      <c r="C13" s="17">
+      <c r="C13" s="23">
         <f>B13</f>
         <v/>
       </c>
@@ -14975,10 +15113,10 @@
           <t>Ponderaciones y sensibilidad</t>
         </is>
       </c>
-      <c r="I13" s="18" t="n">
+      <c r="I13" s="24" t="n">
         <v>2</v>
       </c>
-      <c r="J13" s="16" t="n"/>
+      <c r="J13" s="22" t="n"/>
       <c r="K13" s="15" t="inlineStr">
         <is>
           <t>Pendiente</t>
@@ -15001,10 +15139,10 @@
           <t>S4-T09</t>
         </is>
       </c>
-      <c r="B14" s="16" t="n">
+      <c r="B14" s="22" t="n">
         <v>46332</v>
       </c>
-      <c r="C14" s="17">
+      <c r="C14" s="23">
         <f>B14</f>
         <v/>
       </c>
@@ -15033,10 +15171,10 @@
           <t>Plantillas funcionando</t>
         </is>
       </c>
-      <c r="I14" s="18" t="n">
+      <c r="I14" s="24" t="n">
         <v>2</v>
       </c>
-      <c r="J14" s="16" t="n"/>
+      <c r="J14" s="22" t="n"/>
       <c r="K14" s="15" t="inlineStr">
         <is>
           <t>Pendiente</t>
@@ -15059,10 +15197,10 @@
           <t>S4-T10</t>
         </is>
       </c>
-      <c r="B15" s="16" t="n">
+      <c r="B15" s="22" t="n">
         <v>46332</v>
       </c>
-      <c r="C15" s="17">
+      <c r="C15" s="23">
         <f>B15</f>
         <v/>
       </c>
@@ -15091,10 +15229,10 @@
           <t>Cada precio con enlace y fecha</t>
         </is>
       </c>
-      <c r="I15" s="18" t="n">
+      <c r="I15" s="24" t="n">
         <v>2</v>
       </c>
-      <c r="J15" s="16" t="n"/>
+      <c r="J15" s="22" t="n"/>
       <c r="K15" s="15" t="inlineStr">
         <is>
           <t>Pendiente</t>
@@ -15117,10 +15255,10 @@
           <t>S4-T11</t>
         </is>
       </c>
-      <c r="B16" s="16" t="n">
+      <c r="B16" s="22" t="n">
         <v>46333</v>
       </c>
-      <c r="C16" s="17">
+      <c r="C16" s="23">
         <f>B16</f>
         <v/>
       </c>
@@ -15149,10 +15287,10 @@
           <t>Se ven los pendientes por vendedor</t>
         </is>
       </c>
-      <c r="I16" s="18" t="n">
+      <c r="I16" s="24" t="n">
         <v>3</v>
       </c>
-      <c r="J16" s="16" t="n"/>
+      <c r="J16" s="22" t="n"/>
       <c r="K16" s="15" t="inlineStr">
         <is>
           <t>Pendiente</t>
@@ -15175,10 +15313,10 @@
           <t>S4-T12</t>
         </is>
       </c>
-      <c r="B17" s="16" t="n">
+      <c r="B17" s="22" t="n">
         <v>46333</v>
       </c>
-      <c r="C17" s="17">
+      <c r="C17" s="23">
         <f>B17</f>
         <v/>
       </c>
@@ -15207,10 +15345,10 @@
           <t>Hoja Costos completa</t>
         </is>
       </c>
-      <c r="I17" s="18" t="n">
+      <c r="I17" s="24" t="n">
         <v>3</v>
       </c>
-      <c r="J17" s="16" t="n"/>
+      <c r="J17" s="22" t="n"/>
       <c r="K17" s="15" t="inlineStr">
         <is>
           <t>Pendiente</t>
@@ -15233,10 +15371,10 @@
           <t>S4-T13</t>
         </is>
       </c>
-      <c r="B18" s="16" t="n">
+      <c r="B18" s="22" t="n">
         <v>46334</v>
       </c>
-      <c r="C18" s="17">
+      <c r="C18" s="23">
         <f>B18</f>
         <v/>
       </c>
@@ -15265,10 +15403,10 @@
           <t>Víctor lo leyó</t>
         </is>
       </c>
-      <c r="I18" s="18" t="n">
+      <c r="I18" s="24" t="n">
         <v>0.5</v>
       </c>
-      <c r="J18" s="16" t="n"/>
+      <c r="J18" s="22" t="n"/>
       <c r="K18" s="15" t="inlineStr">
         <is>
           <t>Pendiente</t>
@@ -15291,10 +15429,10 @@
           <t>S4-T14</t>
         </is>
       </c>
-      <c r="B19" s="16" t="n">
+      <c r="B19" s="22" t="n">
         <v>46334</v>
       </c>
-      <c r="C19" s="17">
+      <c r="C19" s="23">
         <f>B19</f>
         <v/>
       </c>
@@ -15323,10 +15461,10 @@
           <t>Diego lo leyó</t>
         </is>
       </c>
-      <c r="I19" s="18" t="n">
+      <c r="I19" s="24" t="n">
         <v>0.5</v>
       </c>
-      <c r="J19" s="16" t="n"/>
+      <c r="J19" s="22" t="n"/>
       <c r="K19" s="15" t="inlineStr">
         <is>
           <t>Pendiente</t>
@@ -15349,10 +15487,10 @@
           <t>S4-T15</t>
         </is>
       </c>
-      <c r="B20" s="16" t="n">
+      <c r="B20" s="22" t="n">
         <v>46334</v>
       </c>
-      <c r="C20" s="17">
+      <c r="C20" s="23">
         <f>B20</f>
         <v/>
       </c>
@@ -15381,10 +15519,10 @@
           <t>El informe del domingo (21:00) sale con la sección nueva</t>
         </is>
       </c>
-      <c r="I20" s="18" t="n">
+      <c r="I20" s="24" t="n">
         <v>1</v>
       </c>
-      <c r="J20" s="16" t="n"/>
+      <c r="J20" s="22" t="n"/>
       <c r="K20" s="15" t="inlineStr">
         <is>
           <t>Pendiente</t>
@@ -15587,10 +15725,10 @@
           <t>S5-T01</t>
         </is>
       </c>
-      <c r="B6" s="16" t="n">
+      <c r="B6" s="22" t="n">
         <v>46335</v>
       </c>
-      <c r="C6" s="17">
+      <c r="C6" s="23">
         <f>B6</f>
         <v/>
       </c>
@@ -15619,10 +15757,10 @@
           <t>Cada supuesto con fuente o dato de campo</t>
         </is>
       </c>
-      <c r="I6" s="18" t="n">
+      <c r="I6" s="24" t="n">
         <v>2</v>
       </c>
-      <c r="J6" s="16" t="n"/>
+      <c r="J6" s="22" t="n"/>
       <c r="K6" s="15" t="inlineStr">
         <is>
           <t>Pendiente</t>
@@ -15645,10 +15783,10 @@
           <t>S5-T02</t>
         </is>
       </c>
-      <c r="B7" s="16" t="n">
+      <c r="B7" s="22" t="n">
         <v>46335</v>
       </c>
-      <c r="C7" s="17">
+      <c r="C7" s="23">
         <f>B7</f>
         <v/>
       </c>
@@ -15677,10 +15815,10 @@
           <t>Demo funcionando</t>
         </is>
       </c>
-      <c r="I7" s="18" t="n">
+      <c r="I7" s="24" t="n">
         <v>2</v>
       </c>
-      <c r="J7" s="16" t="n"/>
+      <c r="J7" s="22" t="n"/>
       <c r="K7" s="15" t="inlineStr">
         <is>
           <t>Pendiente</t>
@@ -15703,10 +15841,10 @@
           <t>S5-T03</t>
         </is>
       </c>
-      <c r="B8" s="16" t="n">
+      <c r="B8" s="22" t="n">
         <v>46336</v>
       </c>
-      <c r="C8" s="17">
+      <c r="C8" s="23">
         <f>B8</f>
         <v/>
       </c>
@@ -15735,10 +15873,10 @@
           <t>Pesimista, base y optimista</t>
         </is>
       </c>
-      <c r="I8" s="18" t="n">
+      <c r="I8" s="24" t="n">
         <v>2</v>
       </c>
-      <c r="J8" s="16" t="n"/>
+      <c r="J8" s="22" t="n"/>
       <c r="K8" s="15" t="inlineStr">
         <is>
           <t>Pendiente</t>
@@ -15761,10 +15899,10 @@
           <t>S5-T04</t>
         </is>
       </c>
-      <c r="B9" s="16" t="n">
+      <c r="B9" s="22" t="n">
         <v>46336</v>
       </c>
-      <c r="C9" s="17">
+      <c r="C9" s="23">
         <f>B9</f>
         <v/>
       </c>
@@ -15793,10 +15931,10 @@
           <t>Demo funcionando</t>
         </is>
       </c>
-      <c r="I9" s="18" t="n">
+      <c r="I9" s="24" t="n">
         <v>2</v>
       </c>
-      <c r="J9" s="16" t="n"/>
+      <c r="J9" s="22" t="n"/>
       <c r="K9" s="15" t="inlineStr">
         <is>
           <t>Pendiente</t>
@@ -15819,10 +15957,10 @@
           <t>S5-T05</t>
         </is>
       </c>
-      <c r="B10" s="16" t="n">
+      <c r="B10" s="22" t="n">
         <v>46337</v>
       </c>
-      <c r="C10" s="17">
+      <c r="C10" s="23">
         <f>B10</f>
         <v/>
       </c>
@@ -15851,10 +15989,10 @@
           <t>Tabla y gráfico</t>
         </is>
       </c>
-      <c r="I10" s="18" t="n">
+      <c r="I10" s="24" t="n">
         <v>2</v>
       </c>
-      <c r="J10" s="16" t="n"/>
+      <c r="J10" s="22" t="n"/>
       <c r="K10" s="15" t="inlineStr">
         <is>
           <t>Pendiente</t>
@@ -15877,10 +16015,10 @@
           <t>S5-T06</t>
         </is>
       </c>
-      <c r="B11" s="16" t="n">
+      <c r="B11" s="22" t="n">
         <v>46337</v>
       </c>
-      <c r="C11" s="17">
+      <c r="C11" s="23">
         <f>B11</f>
         <v/>
       </c>
@@ -15909,10 +16047,10 @@
           <t>Demo funcionando</t>
         </is>
       </c>
-      <c r="I11" s="18" t="n">
+      <c r="I11" s="24" t="n">
         <v>2</v>
       </c>
-      <c r="J11" s="16" t="n"/>
+      <c r="J11" s="22" t="n"/>
       <c r="K11" s="15" t="inlineStr">
         <is>
           <t>Pendiente</t>
@@ -15935,10 +16073,10 @@
           <t>S5-T07</t>
         </is>
       </c>
-      <c r="B12" s="16" t="n">
+      <c r="B12" s="22" t="n">
         <v>46338</v>
       </c>
-      <c r="C12" s="17">
+      <c r="C12" s="23">
         <f>B12</f>
         <v/>
       </c>
@@ -15967,10 +16105,10 @@
           <t>Probabilidad × impacto + mitigación</t>
         </is>
       </c>
-      <c r="I12" s="18" t="n">
+      <c r="I12" s="24" t="n">
         <v>2</v>
       </c>
-      <c r="J12" s="16" t="n"/>
+      <c r="J12" s="22" t="n"/>
       <c r="K12" s="15" t="inlineStr">
         <is>
           <t>Pendiente</t>
@@ -15993,10 +16131,10 @@
           <t>S5-T08</t>
         </is>
       </c>
-      <c r="B13" s="16" t="n">
+      <c r="B13" s="22" t="n">
         <v>46338</v>
       </c>
-      <c r="C13" s="17">
+      <c r="C13" s="23">
         <f>B13</f>
         <v/>
       </c>
@@ -16025,10 +16163,10 @@
           <t>Demo funcionando</t>
         </is>
       </c>
-      <c r="I13" s="18" t="n">
+      <c r="I13" s="24" t="n">
         <v>2</v>
       </c>
-      <c r="J13" s="16" t="n"/>
+      <c r="J13" s="22" t="n"/>
       <c r="K13" s="15" t="inlineStr">
         <is>
           <t>Pendiente</t>
@@ -16051,10 +16189,10 @@
           <t>S5-T09</t>
         </is>
       </c>
-      <c r="B14" s="16" t="n">
+      <c r="B14" s="22" t="n">
         <v>46339</v>
       </c>
-      <c r="C14" s="17">
+      <c r="C14" s="23">
         <f>B14</f>
         <v/>
       </c>
@@ -16083,10 +16221,10 @@
           <t>Artículos del texto oficial</t>
         </is>
       </c>
-      <c r="I14" s="18" t="n">
+      <c r="I14" s="24" t="n">
         <v>2</v>
       </c>
-      <c r="J14" s="16" t="n"/>
+      <c r="J14" s="22" t="n"/>
       <c r="K14" s="15" t="inlineStr">
         <is>
           <t>Pendiente</t>
@@ -16109,10 +16247,10 @@
           <t>S5-T10</t>
         </is>
       </c>
-      <c r="B15" s="16" t="n">
+      <c r="B15" s="22" t="n">
         <v>46339</v>
       </c>
-      <c r="C15" s="17">
+      <c r="C15" s="23">
         <f>B15</f>
         <v/>
       </c>
@@ -16141,10 +16279,10 @@
           <t>Demo de punta a punta</t>
         </is>
       </c>
-      <c r="I15" s="18" t="n">
+      <c r="I15" s="24" t="n">
         <v>2</v>
       </c>
-      <c r="J15" s="16" t="n"/>
+      <c r="J15" s="22" t="n"/>
       <c r="K15" s="15" t="inlineStr">
         <is>
           <t>Pendiente</t>
@@ -16167,10 +16305,10 @@
           <t>S5-T11</t>
         </is>
       </c>
-      <c r="B16" s="16" t="n">
+      <c r="B16" s="22" t="n">
         <v>46340</v>
       </c>
-      <c r="C16" s="17">
+      <c r="C16" s="23">
         <f>B16</f>
         <v/>
       </c>
@@ -16199,10 +16337,10 @@
           <t>Una página con VAN, TIR y propuesta de valor</t>
         </is>
       </c>
-      <c r="I16" s="18" t="n">
+      <c r="I16" s="24" t="n">
         <v>2</v>
       </c>
-      <c r="J16" s="16" t="n"/>
+      <c r="J16" s="22" t="n"/>
       <c r="K16" s="15" t="inlineStr">
         <is>
           <t>Pendiente</t>
@@ -16225,10 +16363,10 @@
           <t>S5-T12</t>
         </is>
       </c>
-      <c r="B17" s="16" t="n">
+      <c r="B17" s="22" t="n">
         <v>46340</v>
       </c>
-      <c r="C17" s="17">
+      <c r="C17" s="23">
         <f>B17</f>
         <v/>
       </c>
@@ -16257,10 +16395,10 @@
           <t>Revisado una vez</t>
         </is>
       </c>
-      <c r="I17" s="18" t="n">
+      <c r="I17" s="24" t="n">
         <v>1.5</v>
       </c>
-      <c r="J17" s="16" t="n"/>
+      <c r="J17" s="22" t="n"/>
       <c r="K17" s="15" t="inlineStr">
         <is>
           <t>Pendiente</t>
@@ -16283,10 +16421,10 @@
           <t>S5-T13</t>
         </is>
       </c>
-      <c r="B18" s="16" t="n">
+      <c r="B18" s="22" t="n">
         <v>46340</v>
       </c>
-      <c r="C18" s="17">
+      <c r="C18" s="23">
         <f>B18</f>
         <v/>
       </c>
@@ -16315,10 +16453,10 @@
           <t>Cada caso con criterio de aceptación</t>
         </is>
       </c>
-      <c r="I18" s="18" t="n">
+      <c r="I18" s="24" t="n">
         <v>3</v>
       </c>
-      <c r="J18" s="16" t="n"/>
+      <c r="J18" s="22" t="n"/>
       <c r="K18" s="15" t="inlineStr">
         <is>
           <t>Pendiente</t>
@@ -16341,10 +16479,10 @@
           <t>S5-T14</t>
         </is>
       </c>
-      <c r="B19" s="16" t="n">
+      <c r="B19" s="22" t="n">
         <v>46341</v>
       </c>
-      <c r="C19" s="17">
+      <c r="C19" s="23">
         <f>B19</f>
         <v/>
       </c>
@@ -16373,10 +16511,10 @@
           <t>Leídos por el otro</t>
         </is>
       </c>
-      <c r="I19" s="18" t="n">
+      <c r="I19" s="24" t="n">
         <v>1</v>
       </c>
-      <c r="J19" s="16" t="n"/>
+      <c r="J19" s="22" t="n"/>
       <c r="K19" s="15" t="inlineStr">
         <is>
           <t>Pendiente</t>
@@ -16399,10 +16537,10 @@
           <t>S5-T15</t>
         </is>
       </c>
-      <c r="B20" s="16" t="n">
+      <c r="B20" s="22" t="n">
         <v>46341</v>
       </c>
-      <c r="C20" s="17">
+      <c r="C20" s="23">
         <f>B20</f>
         <v/>
       </c>
@@ -16431,10 +16569,10 @@
           <t>El informe del domingo (21:00) sale con la sección nueva</t>
         </is>
       </c>
-      <c r="I20" s="18" t="n">
+      <c r="I20" s="24" t="n">
         <v>1</v>
       </c>
-      <c r="J20" s="16" t="n"/>
+      <c r="J20" s="22" t="n"/>
       <c r="K20" s="15" t="inlineStr">
         <is>
           <t>Pendiente</t>
@@ -16637,10 +16775,10 @@
           <t>S6-T01</t>
         </is>
       </c>
-      <c r="B6" s="16" t="n">
+      <c r="B6" s="22" t="n">
         <v>46342</v>
       </c>
-      <c r="C6" s="17">
+      <c r="C6" s="23">
         <f>B6</f>
         <v/>
       </c>
@@ -16669,10 +16807,10 @@
           <t>Máx. 15 diapositivas</t>
         </is>
       </c>
-      <c r="I6" s="18" t="n">
+      <c r="I6" s="24" t="n">
         <v>2</v>
       </c>
-      <c r="J6" s="16" t="n"/>
+      <c r="J6" s="22" t="n"/>
       <c r="K6" s="15" t="inlineStr">
         <is>
           <t>Pendiente</t>
@@ -16695,10 +16833,10 @@
           <t>S6-T02</t>
         </is>
       </c>
-      <c r="B7" s="16" t="n">
+      <c r="B7" s="22" t="n">
         <v>46343</v>
       </c>
-      <c r="C7" s="17">
+      <c r="C7" s="23">
         <f>B7</f>
         <v/>
       </c>
@@ -16727,10 +16865,10 @@
           <t>Dura ≤20 min</t>
         </is>
       </c>
-      <c r="I7" s="18" t="n">
+      <c r="I7" s="24" t="n">
         <v>1</v>
       </c>
-      <c r="J7" s="16" t="n"/>
+      <c r="J7" s="22" t="n"/>
       <c r="K7" s="15" t="inlineStr">
         <is>
           <t>Pendiente</t>
@@ -16753,10 +16891,10 @@
           <t>S6-T03</t>
         </is>
       </c>
-      <c r="B8" s="16" t="n">
+      <c r="B8" s="22" t="n">
         <v>46343</v>
       </c>
-      <c r="C8" s="17">
+      <c r="C8" s="23">
         <f>B8</f>
         <v/>
       </c>
@@ -16785,10 +16923,10 @@
           <t>3 corridas seguidas sin error</t>
         </is>
       </c>
-      <c r="I8" s="18" t="n">
+      <c r="I8" s="24" t="n">
         <v>1</v>
       </c>
-      <c r="J8" s="16" t="n"/>
+      <c r="J8" s="22" t="n"/>
       <c r="K8" s="15" t="inlineStr">
         <is>
           <t>Pendiente</t>
@@ -16811,10 +16949,10 @@
           <t>S6-T04</t>
         </is>
       </c>
-      <c r="B9" s="16" t="n">
+      <c r="B9" s="22" t="n">
         <v>46344</v>
       </c>
-      <c r="C9" s="17">
+      <c r="C9" s="23">
         <f>B9</f>
         <v/>
       </c>
@@ -16843,10 +16981,10 @@
           <t>Reunión realizada</t>
         </is>
       </c>
-      <c r="I9" s="18" t="n">
+      <c r="I9" s="24" t="n">
         <v>1.5</v>
       </c>
-      <c r="J9" s="16" t="n"/>
+      <c r="J9" s="22" t="n"/>
       <c r="K9" s="15" t="inlineStr">
         <is>
           <t>Pendiente</t>
@@ -16873,10 +17011,10 @@
           <t>S6-T05</t>
         </is>
       </c>
-      <c r="B10" s="16" t="n">
+      <c r="B10" s="22" t="n">
         <v>46344</v>
       </c>
-      <c r="C10" s="17">
+      <c r="C10" s="23">
         <f>B10</f>
         <v/>
       </c>
@@ -16905,10 +17043,10 @@
           <t>Observaciones con responsable y plazo</t>
         </is>
       </c>
-      <c r="I10" s="18" t="n">
+      <c r="I10" s="24" t="n">
         <v>0.5</v>
       </c>
-      <c r="J10" s="16" t="n"/>
+      <c r="J10" s="22" t="n"/>
       <c r="K10" s="15" t="inlineStr">
         <is>
           <t>Pendiente</t>
@@ -16931,10 +17069,10 @@
           <t>S6-T06</t>
         </is>
       </c>
-      <c r="B11" s="16" t="n">
+      <c r="B11" s="22" t="n">
         <v>46345</v>
       </c>
-      <c r="C11" s="17">
+      <c r="C11" s="23">
         <f>B11</f>
         <v/>
       </c>
@@ -16963,10 +17101,10 @@
           <t>Fechas, participantes y mediciones definidos</t>
         </is>
       </c>
-      <c r="I11" s="18" t="n">
+      <c r="I11" s="24" t="n">
         <v>2</v>
       </c>
-      <c r="J11" s="16" t="n"/>
+      <c r="J11" s="22" t="n"/>
       <c r="K11" s="15" t="inlineStr">
         <is>
           <t>Pendiente</t>
@@ -16989,10 +17127,10 @@
           <t>S6-T07</t>
         </is>
       </c>
-      <c r="B12" s="16" t="n">
+      <c r="B12" s="22" t="n">
         <v>46345</v>
       </c>
-      <c r="C12" s="17">
+      <c r="C12" s="23">
         <f>B12</f>
         <v/>
       </c>
@@ -17021,10 +17159,10 @@
           <t>Etiqueta de versión en el repositorio</t>
         </is>
       </c>
-      <c r="I12" s="18" t="n">
+      <c r="I12" s="24" t="n">
         <v>2</v>
       </c>
-      <c r="J12" s="16" t="n"/>
+      <c r="J12" s="22" t="n"/>
       <c r="K12" s="15" t="inlineStr">
         <is>
           <t>Pendiente</t>
@@ -17047,10 +17185,10 @@
           <t>S6-T08</t>
         </is>
       </c>
-      <c r="B13" s="16" t="n">
+      <c r="B13" s="22" t="n">
         <v>46346</v>
       </c>
-      <c r="C13" s="17">
+      <c r="C13" s="23">
         <f>B13</f>
         <v/>
       </c>
@@ -17079,10 +17217,10 @@
           <t>Respuesta recibida</t>
         </is>
       </c>
-      <c r="I13" s="18" t="n">
+      <c r="I13" s="24" t="n">
         <v>1</v>
       </c>
-      <c r="J13" s="16" t="n"/>
+      <c r="J13" s="22" t="n"/>
       <c r="K13" s="15" t="inlineStr">
         <is>
           <t>Pendiente</t>
@@ -17105,10 +17243,10 @@
           <t>S6-T09</t>
         </is>
       </c>
-      <c r="B14" s="16" t="n">
+      <c r="B14" s="22" t="n">
         <v>46346</v>
       </c>
-      <c r="C14" s="17">
+      <c r="C14" s="23">
         <f>B14</f>
         <v/>
       </c>
@@ -17137,10 +17275,10 @@
           <t>Los 3 casos pasan</t>
         </is>
       </c>
-      <c r="I14" s="18" t="n">
+      <c r="I14" s="24" t="n">
         <v>2</v>
       </c>
-      <c r="J14" s="16" t="n"/>
+      <c r="J14" s="22" t="n"/>
       <c r="K14" s="15" t="inlineStr">
         <is>
           <t>Pendiente</t>
@@ -17163,10 +17301,10 @@
           <t>S6-T10</t>
         </is>
       </c>
-      <c r="B15" s="16" t="n">
+      <c r="B15" s="22" t="n">
         <v>46347</v>
       </c>
-      <c r="C15" s="17">
+      <c r="C15" s="23">
         <f>B15</f>
         <v/>
       </c>
@@ -17195,10 +17333,10 @@
           <t>Observaciones cerradas</t>
         </is>
       </c>
-      <c r="I15" s="18" t="n">
+      <c r="I15" s="24" t="n">
         <v>3</v>
       </c>
-      <c r="J15" s="16" t="n"/>
+      <c r="J15" s="22" t="n"/>
       <c r="K15" s="15" t="inlineStr">
         <is>
           <t>Pendiente</t>
@@ -17221,10 +17359,10 @@
           <t>S6-T11</t>
         </is>
       </c>
-      <c r="B16" s="16" t="n">
+      <c r="B16" s="22" t="n">
         <v>46347</v>
       </c>
-      <c r="C16" s="17">
+      <c r="C16" s="23">
         <f>B16</f>
         <v/>
       </c>
@@ -17253,10 +17391,10 @@
           <t>Observaciones cerradas</t>
         </is>
       </c>
-      <c r="I16" s="18" t="n">
+      <c r="I16" s="24" t="n">
         <v>3</v>
       </c>
-      <c r="J16" s="16" t="n"/>
+      <c r="J16" s="22" t="n"/>
       <c r="K16" s="15" t="inlineStr">
         <is>
           <t>Pendiente</t>
@@ -17279,10 +17417,10 @@
           <t>S6-T12</t>
         </is>
       </c>
-      <c r="B17" s="16" t="n">
+      <c r="B17" s="22" t="n">
         <v>46348</v>
       </c>
-      <c r="C17" s="17">
+      <c r="C17" s="23">
         <f>B17</f>
         <v/>
       </c>
@@ -17311,10 +17449,10 @@
           <t>El informe del domingo (21:00) sale con la sección nueva</t>
         </is>
       </c>
-      <c r="I17" s="18" t="n">
+      <c r="I17" s="24" t="n">
         <v>1</v>
       </c>
-      <c r="J17" s="16" t="n"/>
+      <c r="J17" s="22" t="n"/>
       <c r="K17" s="15" t="inlineStr">
         <is>
           <t>Pendiente</t>

--- a/11_Planificacion/Cronograma_Tesis.xlsx
+++ b/11_Planificacion/Cronograma_Tesis.xlsx
@@ -3978,6 +3978,7 @@
         <v/>
       </c>
     </row>
+    <row r="4"/>
     <row r="5" ht="30" customHeight="1">
       <c r="A5" s="14" t="inlineStr">
         <is>
@@ -4396,7 +4397,11 @@
           <t>S10-02 (#47)</t>
         </is>
       </c>
-      <c r="N11" s="15" t="inlineStr"/>
+      <c r="N11" s="15" t="inlineStr">
+        <is>
+          <t>Escenario B confirmado (entrega 4-ene-2027): las tareas ✂ se mantienen</t>
+        </is>
+      </c>
     </row>
     <row r="12">
       <c r="A12" s="15" t="inlineStr">
@@ -4622,6 +4627,7 @@
         <v/>
       </c>
     </row>
+    <row r="4"/>
     <row r="5" ht="30" customHeight="1">
       <c r="A5" s="14" t="inlineStr">
         <is>
@@ -5040,7 +5046,11 @@
           <t>H-01 (#48)</t>
         </is>
       </c>
-      <c r="N11" s="15" t="inlineStr"/>
+      <c r="N11" s="15" t="inlineStr">
+        <is>
+          <t>Última lectura antes de la fecha límite del lunes 4-ene-2027</t>
+        </is>
+      </c>
     </row>
   </sheetData>
   <autoFilter ref="A5:N11"/>
@@ -5150,6 +5160,7 @@
         <v/>
       </c>
     </row>
+    <row r="4"/>
     <row r="5" ht="30" customHeight="1">
       <c r="A5" s="14" t="inlineStr">
         <is>
@@ -5278,7 +5289,11 @@
           <t>E-01 (#49)</t>
         </is>
       </c>
-      <c r="N6" s="15" t="inlineStr"/>
+      <c r="N6" s="15" t="inlineStr">
+        <is>
+          <t>FECHA LÍMITE (D5, Víctor 18-oct): el lunes 4-ene-2027 el documento final está completo y listo para la revisión de la tutora</t>
+        </is>
+      </c>
     </row>
     <row r="7">
       <c r="A7" s="15" t="inlineStr">
@@ -6768,7 +6783,6 @@
         <v/>
       </c>
     </row>
-    <row r="4"/>
     <row r="5" ht="30" customHeight="1">
       <c r="A5" s="14" t="inlineStr">
         <is>
@@ -12348,7 +12362,6 @@
         <v/>
       </c>
     </row>
-    <row r="4"/>
     <row r="5" ht="30" customHeight="1">
       <c r="A5" s="14" t="inlineStr">
         <is>

--- a/11_Planificacion/Cronograma_Tesis.xlsx
+++ b/11_Planificacion/Cronograma_Tesis.xlsx
@@ -3978,7 +3978,6 @@
         <v/>
       </c>
     </row>
-    <row r="4"/>
     <row r="5" ht="30" customHeight="1">
       <c r="A5" s="14" t="inlineStr">
         <is>
@@ -4627,7 +4626,6 @@
         <v/>
       </c>
     </row>
-    <row r="4"/>
     <row r="5" ht="30" customHeight="1">
       <c r="A5" s="14" t="inlineStr">
         <is>
@@ -5160,7 +5158,6 @@
         <v/>
       </c>
     </row>
-    <row r="4"/>
     <row r="5" ht="30" customHeight="1">
       <c r="A5" s="14" t="inlineStr">
         <is>
@@ -12478,7 +12475,7 @@
       <c r="J6" s="22" t="n"/>
       <c r="K6" s="15" t="inlineStr">
         <is>
-          <t>Pendiente</t>
+          <t>En curso</t>
         </is>
       </c>
       <c r="L6" s="15">
@@ -12492,7 +12489,7 @@
       </c>
       <c r="N6" s="15" t="inlineStr">
         <is>
-          <t>Bloque doble con: bajar a mano los PDF de la matriz (Oldroyd, Pollitt, Galan, Nyqvist, Lewis y Sauro, Auernhammer) → Claude los verifica</t>
+          <t>Bloque doble con: bajar a mano los PDF de la matriz (Oldroyd, Pollitt, Galan, Nyqvist, Lewis y Sauro, Auernhammer) → Claude los verifica · 19-oct: Cap. I parte 1 v0.1 hecha por Claude (control de cambios); Víctor revisa. PDF a mano: esta noche</t>
         </is>
       </c>
     </row>
@@ -12602,7 +12599,7 @@
       <c r="J8" s="22" t="n"/>
       <c r="K8" s="15" t="inlineStr">
         <is>
-          <t>Pendiente</t>
+          <t>En curso</t>
         </is>
       </c>
       <c r="L8" s="15">
@@ -12616,7 +12613,7 @@
       </c>
       <c r="N8" s="15" t="inlineStr">
         <is>
-          <t>Bloque doble con: fuentes de CRM A21–A27 (Claude busca y verifica, Víctor revisa)</t>
+          <t>Bloque doble con: fuentes de CRM A21–A27 (Claude busca y verifica, Víctor revisa) · Adelantada al 19-oct: Cap. I parte 2 v0.1 (justificación, objetivos, metas, alcance); Víctor revisa</t>
         </is>
       </c>
     </row>
@@ -12726,7 +12723,7 @@
       <c r="J10" s="22" t="n"/>
       <c r="K10" s="15" t="inlineStr">
         <is>
-          <t>Pendiente</t>
+          <t>En curso</t>
         </is>
       </c>
       <c r="L10" s="15">
@@ -12740,7 +12737,7 @@
       </c>
       <c r="N10" s="15" t="inlineStr">
         <is>
-          <t>Bloque doble con: censo y métodos A40–A41 (biblioteca UPS: Hernández-Sampieri y Mendoza, 2018)</t>
+          <t>Bloque doble con: censo y métodos A40–A41 (biblioteca UPS: Hernández-Sampieri y Mendoza, 2018) · Adelantada al 19-oct: Cap. II v0.1 con lo verificado (7 fuentes nuevas). Falta CRM móvil (A21–A25) y clásicos de KM</t>
         </is>
       </c>
     </row>
@@ -12850,7 +12847,7 @@
       <c r="J12" s="22" t="n"/>
       <c r="K12" s="15" t="inlineStr">
         <is>
-          <t>Pendiente</t>
+          <t>En curso</t>
         </is>
       </c>
       <c r="L12" s="15">
@@ -12864,7 +12861,7 @@
       </c>
       <c r="N12" s="15" t="inlineStr">
         <is>
-          <t>Bloque doble con: A44 (Ley de Comercio Electrónico) y A30 (blockchain)</t>
+          <t>Bloque doble con: A44 (Ley de Comercio Electrónico) y A30 (blockchain) · Adelantada al 19-oct: va en el mismo Cap. II v0.1 (RAG, normativa). Faltan Lewis 2020, Kleppmann, SHA-256, A44</t>
         </is>
       </c>
     </row>
@@ -12967,10 +12964,12 @@
       <c r="I14" s="24" t="n">
         <v>1</v>
       </c>
-      <c r="J14" s="22" t="n"/>
+      <c r="J14" s="22" t="n">
+        <v>46314</v>
+      </c>
       <c r="K14" s="15" t="inlineStr">
         <is>
-          <t>Pendiente</t>
+          <t>Hecho</t>
         </is>
       </c>
       <c r="L14" s="15">
@@ -12982,7 +12981,11 @@
           <t>S2-02 (#14)</t>
         </is>
       </c>
-      <c r="N14" s="15" t="inlineStr"/>
+      <c r="N14" s="15" t="inlineStr">
+        <is>
+          <t>19-oct: 4 fichas nuevas de IA (rodriguez_2025, chatterjee_2023a, bohm_2026, hernandezvega_2026) + 10 de CTX-IA ya verificadas</t>
+        </is>
+      </c>
     </row>
     <row r="15">
       <c r="A15" s="15" t="inlineStr">
@@ -13028,7 +13031,7 @@
       <c r="J15" s="22" t="n"/>
       <c r="K15" s="15" t="inlineStr">
         <is>
-          <t>Pendiente</t>
+          <t>En curso</t>
         </is>
       </c>
       <c r="L15" s="15">
@@ -13040,7 +13043,11 @@
           <t>S2-07 (#58)</t>
         </is>
       </c>
-      <c r="N15" s="15" t="inlineStr"/>
+      <c r="N15" s="15" t="inlineStr">
+        <is>
+          <t>Adelantada al 19-oct: lienzo v0.1 (propuesta de valor para Torvesa + TEAMSLASH como anexo, D7); Víctor revisa</t>
+        </is>
+      </c>
     </row>
     <row r="16">
       <c r="A16" s="15" t="inlineStr">
@@ -13144,7 +13151,7 @@
       <c r="J17" s="22" t="n"/>
       <c r="K17" s="15" t="inlineStr">
         <is>
-          <t>Pendiente</t>
+          <t>En curso</t>
         </is>
       </c>
       <c r="L17" s="15">
@@ -13156,7 +13163,11 @@
           <t>S2-03 (#15)</t>
         </is>
       </c>
-      <c r="N17" s="15" t="inlineStr"/>
+      <c r="N17" s="15" t="inlineStr">
+        <is>
+          <t>Adelantada al 19-oct: Cap. III completo v0.1 (partes 1 y 2); Víctor revisa</t>
+        </is>
+      </c>
     </row>
     <row r="18">
       <c r="A18" s="15" t="inlineStr">
@@ -13202,7 +13213,7 @@
       <c r="J18" s="22" t="n"/>
       <c r="K18" s="15" t="inlineStr">
         <is>
-          <t>Pendiente</t>
+          <t>En curso</t>
         </is>
       </c>
       <c r="L18" s="15">
@@ -13214,7 +13225,11 @@
           <t>S2-01 (#13)</t>
         </is>
       </c>
-      <c r="N18" s="15" t="inlineStr"/>
+      <c r="N18" s="15" t="inlineStr">
+        <is>
+          <t>Adelantada al 19-oct: 06_Capitulos/2026-10-19_Resumen_Cap1.md; Víctor lo revisa y lo envía</t>
+        </is>
+      </c>
     </row>
     <row r="19">
       <c r="A19" s="15" t="inlineStr">
@@ -13376,7 +13391,7 @@
       <c r="J21" s="22" t="n"/>
       <c r="K21" s="15" t="inlineStr">
         <is>
-          <t>Pendiente</t>
+          <t>En curso</t>
         </is>
       </c>
       <c r="L21" s="15">
@@ -13388,7 +13403,11 @@
           <t>S2-03 (#15)</t>
         </is>
       </c>
-      <c r="N21" s="15" t="inlineStr"/>
+      <c r="N21" s="15" t="inlineStr">
+        <is>
+          <t>Adelantada al 19-oct: va en el mismo Cap. III v0.1; Víctor revisa</t>
+        </is>
+      </c>
     </row>
     <row r="22">
       <c r="A22" s="15" t="inlineStr">

--- a/11_Planificacion/Cronograma_Tesis.xlsx
+++ b/11_Planificacion/Cronograma_Tesis.xlsx
@@ -45,11 +45,12 @@
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <numFmts count="4">
+  <numFmts count="5">
     <numFmt numFmtId="164" formatCode="dd-mmm"/>
     <numFmt numFmtId="165" formatCode="dddd"/>
     <numFmt numFmtId="166" formatCode="0.0"/>
     <numFmt numFmtId="167" formatCode="dd-mmm-yy"/>
+    <numFmt numFmtId="168" formatCode="yyyy-mm-dd"/>
   </numFmts>
   <fonts count="12">
     <font>
@@ -156,7 +157,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="27">
+  <cellXfs count="28">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="2" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
@@ -202,6 +203,9 @@
     </xf>
     <xf numFmtId="167" fontId="7" fillId="0" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="165" fontId="7" fillId="0" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="168" fontId="7" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment vertical="top" wrapText="1"/>
+    </xf>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0" hidden="0"/>
@@ -12472,10 +12476,12 @@
       <c r="I6" s="24" t="n">
         <v>2</v>
       </c>
-      <c r="J6" s="22" t="n"/>
+      <c r="J6" s="27" t="n">
+        <v>46315</v>
+      </c>
       <c r="K6" s="15" t="inlineStr">
         <is>
-          <t>En curso</t>
+          <t>Hecho</t>
         </is>
       </c>
       <c r="L6" s="15">
@@ -12489,7 +12495,7 @@
       </c>
       <c r="N6" s="15" t="inlineStr">
         <is>
-          <t>Bloque doble con: bajar a mano los PDF de la matriz (Oldroyd, Pollitt, Galan, Nyqvist, Lewis y Sauro, Auernhammer) → Claude los verifica · 19-oct: Cap. I parte 1 v0.1 hecha por Claude (control de cambios); Víctor revisa. PDF a mano: esta noche</t>
+          <t>Bloque doble con: bajar a mano los PDF de la matriz (Oldroyd, Pollitt, Galan, Nyqvist, Lewis y Sauro, Auernhammer) → Claude los verifica · 19-oct: Cap. I parte 1 v0.1 hecha por Claude (control de cambios); Víctor revisa. PDF a mano: esta noche · 20-oct: Víctor aprobó la v0.1; v0.2 en 06_Capitulos/2026-10-20_Cap1_Introduccion_p1_v0.2.docx</t>
         </is>
       </c>
     </row>
@@ -12596,10 +12602,12 @@
       <c r="I8" s="24" t="n">
         <v>2</v>
       </c>
-      <c r="J8" s="22" t="n"/>
+      <c r="J8" s="27" t="n">
+        <v>46315</v>
+      </c>
       <c r="K8" s="15" t="inlineStr">
         <is>
-          <t>En curso</t>
+          <t>Hecho</t>
         </is>
       </c>
       <c r="L8" s="15">
@@ -12613,7 +12621,7 @@
       </c>
       <c r="N8" s="15" t="inlineStr">
         <is>
-          <t>Bloque doble con: fuentes de CRM A21–A27 (Claude busca y verifica, Víctor revisa) · Adelantada al 19-oct: Cap. I parte 2 v0.1 (justificación, objetivos, metas, alcance); Víctor revisa</t>
+          <t>Bloque doble con: fuentes de CRM A21–A27 (Claude busca y verifica, Víctor revisa) · Adelantada al 19-oct: Cap. I parte 2 v0.1 (justificación, objetivos, metas, alcance); Víctor revisa · 20-oct: Víctor aprobó la v0.1; v0.2 con vacíos A28/A29 documentados (2026-10-20_Cap1_Introduccion_p2_v0.2.docx)</t>
         </is>
       </c>
     </row>
@@ -12720,10 +12728,12 @@
       <c r="I10" s="24" t="n">
         <v>2</v>
       </c>
-      <c r="J10" s="22" t="n"/>
+      <c r="J10" s="27" t="n">
+        <v>46315</v>
+      </c>
       <c r="K10" s="15" t="inlineStr">
         <is>
-          <t>En curso</t>
+          <t>Hecho</t>
         </is>
       </c>
       <c r="L10" s="15">
@@ -12737,7 +12747,7 @@
       </c>
       <c r="N10" s="15" t="inlineStr">
         <is>
-          <t>Bloque doble con: censo y métodos A40–A41 (biblioteca UPS: Hernández-Sampieri y Mendoza, 2018) · Adelantada al 19-oct: Cap. II v0.1 con lo verificado (7 fuentes nuevas). Falta CRM móvil (A21–A25) y clásicos de KM</t>
+          <t>Bloque doble con: censo y métodos A40–A41 (biblioteca UPS: Hernández-Sampieri y Mendoza, 2018) · Adelantada al 19-oct: Cap. II v0.1 con lo verificado (7 fuentes nuevas). Falta CRM móvil (A21–A25) y clásicos de KM · 20-oct: Víctor aprobó la v0.1; v0.2 con TEAMSLASH como antecedente propio (DEC-17)</t>
         </is>
       </c>
     </row>
@@ -12844,10 +12854,12 @@
       <c r="I12" s="24" t="n">
         <v>2</v>
       </c>
-      <c r="J12" s="22" t="n"/>
+      <c r="J12" s="27" t="n">
+        <v>46315</v>
+      </c>
       <c r="K12" s="15" t="inlineStr">
         <is>
-          <t>En curso</t>
+          <t>Hecho</t>
         </is>
       </c>
       <c r="L12" s="15">
@@ -12861,7 +12873,7 @@
       </c>
       <c r="N12" s="15" t="inlineStr">
         <is>
-          <t>Bloque doble con: A44 (Ley de Comercio Electrónico) y A30 (blockchain) · Adelantada al 19-oct: va en el mismo Cap. II v0.1 (RAG, normativa). Faltan Lewis 2020, Kleppmann, SHA-256, A44</t>
+          <t>Bloque doble con: A44 (Ley de Comercio Electrónico) y A30 (blockchain) · Adelantada al 19-oct: va en el mismo Cap. II v0.1 (RAG, normativa). Faltan Lewis 2020, Kleppmann, SHA-256, A44 · 20-oct: v0.2 con norma SHA-256 (NIST 2015) y vacíos reformulados (2026-10-20_Cap2_Marco_Teorico_v0.2.docx)</t>
         </is>
       </c>
     </row>
@@ -13028,10 +13040,12 @@
       <c r="I15" s="24" t="n">
         <v>1</v>
       </c>
-      <c r="J15" s="22" t="n"/>
+      <c r="J15" s="27" t="n">
+        <v>46315</v>
+      </c>
       <c r="K15" s="15" t="inlineStr">
         <is>
-          <t>En curso</t>
+          <t>Hecho</t>
         </is>
       </c>
       <c r="L15" s="15">
@@ -13045,7 +13059,7 @@
       </c>
       <c r="N15" s="15" t="inlineStr">
         <is>
-          <t>Adelantada al 19-oct: lienzo v0.1 (propuesta de valor para Torvesa + TEAMSLASH como anexo, D7); Víctor revisa</t>
+          <t>Adelantada al 19-oct: lienzo v0.1 (propuesta de valor para Torvesa + TEAMSLASH como anexo, D7); Víctor revisa · 20-oct: lienzo v0.2 con DEC-16 (bóveda en Estándar, IA solo en Premium)</t>
         </is>
       </c>
     </row>
@@ -13148,10 +13162,12 @@
       <c r="I17" s="24" t="n">
         <v>3</v>
       </c>
-      <c r="J17" s="22" t="n"/>
+      <c r="J17" s="27" t="n">
+        <v>46315</v>
+      </c>
       <c r="K17" s="15" t="inlineStr">
         <is>
-          <t>En curso</t>
+          <t>Hecho</t>
         </is>
       </c>
       <c r="L17" s="15">
@@ -13165,7 +13181,7 @@
       </c>
       <c r="N17" s="15" t="inlineStr">
         <is>
-          <t>Adelantada al 19-oct: Cap. III completo v0.1 (partes 1 y 2); Víctor revisa</t>
+          <t>Adelantada al 19-oct: Cap. III completo v0.1 (partes 1 y 2); Víctor revisa · 20-oct: Víctor aprobó la v0.1; v0.2 (2026-10-20_Cap3_Metodologia_v0.2.docx)</t>
         </is>
       </c>
     </row>
@@ -13388,10 +13404,12 @@
       <c r="I21" s="24" t="n">
         <v>2</v>
       </c>
-      <c r="J21" s="22" t="n"/>
+      <c r="J21" s="27" t="n">
+        <v>46315</v>
+      </c>
       <c r="K21" s="15" t="inlineStr">
         <is>
-          <t>En curso</t>
+          <t>Hecho</t>
         </is>
       </c>
       <c r="L21" s="15">
@@ -13405,7 +13423,7 @@
       </c>
       <c r="N21" s="15" t="inlineStr">
         <is>
-          <t>Adelantada al 19-oct: va en el mismo Cap. III v0.1; Víctor revisa</t>
+          <t>Adelantada al 19-oct: va en el mismo Cap. III v0.1; Víctor revisa · 20-oct: va en el mismo Cap. III v0.2</t>
         </is>
       </c>
     </row>

--- a/11_Planificacion/Cronograma_Tesis.xlsx
+++ b/11_Planificacion/Cronograma_Tesis.xlsx
@@ -27,8 +27,8 @@
   <definedNames>
     <definedName name="_xlnm._FilterDatabase" localSheetId="2" hidden="1">'S1'!$A$5:$N$32</definedName>
     <definedName name="_xlnm._FilterDatabase" localSheetId="4" hidden="1">'S2'!$A$5:$N$23</definedName>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="5" hidden="1">'S3'!$A$5:$N$19</definedName>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="6" hidden="1">'S4'!$A$5:$N$20</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="5" hidden="1">'S3'!$A$5:$N$24</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="6" hidden="1">'S4'!$A$5:$N$22</definedName>
     <definedName name="_xlnm._FilterDatabase" localSheetId="7" hidden="1">'S5'!$A$5:$N$20</definedName>
     <definedName name="_xlnm._FilterDatabase" localSheetId="8" hidden="1">'S6'!$A$5:$N$17</definedName>
     <definedName name="_xlnm._FilterDatabase" localSheetId="9" hidden="1">'S7'!$A$5:$N$19</definedName>
@@ -45,12 +45,13 @@
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <numFmts count="5">
+  <numFmts count="6">
     <numFmt numFmtId="164" formatCode="dd-mmm"/>
     <numFmt numFmtId="165" formatCode="dddd"/>
     <numFmt numFmtId="166" formatCode="0.0"/>
     <numFmt numFmtId="167" formatCode="dd-mmm-yy"/>
     <numFmt numFmtId="168" formatCode="yyyy-mm-dd"/>
+    <numFmt numFmtId="169" formatCode="yyyy-mm-dd h:mm:ss"/>
   </numFmts>
   <fonts count="12">
     <font>
@@ -6029,6 +6030,7 @@
       <c r="M2" s="2" t="n"/>
       <c r="N2" s="2" t="n"/>
     </row>
+    <row r="3"/>
     <row r="4">
       <c r="A4" s="6" t="inlineStr">
         <is>
@@ -6181,11 +6183,11 @@
         </is>
       </c>
       <c r="C7" s="7">
-        <f>COUNTA('S3'!D6:D19)-COUNTIF('S3'!K6:K19,"Cancelado")</f>
+        <f>COUNTA('S3'!D6:D24)-COUNTIF('S3'!K6:K24,"Cancelado")</f>
         <v/>
       </c>
       <c r="D7" s="7">
-        <f>COUNTIF('S3'!K6:K19,"Hecho")</f>
+        <f>COUNTIF('S3'!K6:K24,"Hecho")</f>
         <v/>
       </c>
       <c r="E7" s="8">
@@ -6193,23 +6195,23 @@
         <v/>
       </c>
       <c r="F7" s="8">
-        <f>IFERROR((COUNTIFS('S3'!E6:E19,"Víctor",'S3'!K6:K19,"Hecho")+COUNTIFS('S3'!E6:E19,"Ambos",'S3'!K6:K19,"Hecho"))/(COUNTIF('S3'!E6:E19,"Víctor")+COUNTIF('S3'!E6:E19,"Ambos")),0)</f>
+        <f>IFERROR((COUNTIFS('S3'!E6:E24,"Víctor",'S3'!K6:K24,"Hecho")+COUNTIFS('S3'!E6:E24,"Ambos",'S3'!K6:K24,"Hecho"))/(COUNTIF('S3'!E6:E24,"Víctor")+COUNTIF('S3'!E6:E24,"Ambos")),0)</f>
         <v/>
       </c>
       <c r="G7" s="8">
-        <f>IFERROR((COUNTIFS('S3'!E6:E19,"Diego",'S3'!K6:K19,"Hecho")+COUNTIFS('S3'!E6:E19,"Ambos",'S3'!K6:K19,"Hecho"))/(COUNTIF('S3'!E6:E19,"Diego")+COUNTIF('S3'!E6:E19,"Ambos")),0)</f>
+        <f>IFERROR((COUNTIFS('S3'!E6:E24,"Diego",'S3'!K6:K24,"Hecho")+COUNTIFS('S3'!E6:E24,"Ambos",'S3'!K6:K24,"Hecho"))/(COUNTIF('S3'!E6:E24,"Diego")+COUNTIF('S3'!E6:E24,"Ambos")),0)</f>
         <v/>
       </c>
       <c r="H7" s="7">
-        <f>SUMIF('S3'!E6:E19,"Víctor",'S3'!I6:I19)+SUMIF('S3'!E6:E19,"Ambos",'S3'!I6:I19)</f>
+        <f>SUMIF('S3'!E6:E24,"Víctor",'S3'!I6:I24)+SUMIF('S3'!E6:E24,"Ambos",'S3'!I6:I24)</f>
         <v/>
       </c>
       <c r="I7" s="7">
-        <f>SUMIF('S3'!E6:E19,"Diego",'S3'!I6:I19)+SUMIF('S3'!E6:E19,"Ambos",'S3'!I6:I19)</f>
+        <f>SUMIF('S3'!E6:E24,"Diego",'S3'!I6:I24)+SUMIF('S3'!E6:E24,"Ambos",'S3'!I6:I24)</f>
         <v/>
       </c>
       <c r="J7" s="7">
-        <f>COUNTIF('S3'!L6:L19,"&gt;0")</f>
+        <f>COUNTIF('S3'!L6:L24,"&gt;0")</f>
         <v/>
       </c>
     </row>
@@ -6225,11 +6227,11 @@
         </is>
       </c>
       <c r="C8" s="7">
-        <f>COUNTA('S4'!D6:D20)-COUNTIF('S4'!K6:K20,"Cancelado")</f>
+        <f>COUNTA('S4'!D6:D22)-COUNTIF('S4'!K6:K22,"Cancelado")</f>
         <v/>
       </c>
       <c r="D8" s="7">
-        <f>COUNTIF('S4'!K6:K20,"Hecho")</f>
+        <f>COUNTIF('S4'!K6:K22,"Hecho")</f>
         <v/>
       </c>
       <c r="E8" s="8">
@@ -6237,23 +6239,23 @@
         <v/>
       </c>
       <c r="F8" s="8">
-        <f>IFERROR((COUNTIFS('S4'!E6:E20,"Víctor",'S4'!K6:K20,"Hecho")+COUNTIFS('S4'!E6:E20,"Ambos",'S4'!K6:K20,"Hecho"))/(COUNTIF('S4'!E6:E20,"Víctor")+COUNTIF('S4'!E6:E20,"Ambos")),0)</f>
+        <f>IFERROR((COUNTIFS('S4'!E6:E22,"Víctor",'S4'!K6:K22,"Hecho")+COUNTIFS('S4'!E6:E22,"Ambos",'S4'!K6:K22,"Hecho"))/(COUNTIF('S4'!E6:E22,"Víctor")+COUNTIF('S4'!E6:E22,"Ambos")),0)</f>
         <v/>
       </c>
       <c r="G8" s="8">
-        <f>IFERROR((COUNTIFS('S4'!E6:E20,"Diego",'S4'!K6:K20,"Hecho")+COUNTIFS('S4'!E6:E20,"Ambos",'S4'!K6:K20,"Hecho"))/(COUNTIF('S4'!E6:E20,"Diego")+COUNTIF('S4'!E6:E20,"Ambos")),0)</f>
+        <f>IFERROR((COUNTIFS('S4'!E6:E22,"Diego",'S4'!K6:K22,"Hecho")+COUNTIFS('S4'!E6:E22,"Ambos",'S4'!K6:K22,"Hecho"))/(COUNTIF('S4'!E6:E22,"Diego")+COUNTIF('S4'!E6:E22,"Ambos")),0)</f>
         <v/>
       </c>
       <c r="H8" s="7">
-        <f>SUMIF('S4'!E6:E20,"Víctor",'S4'!I6:I20)+SUMIF('S4'!E6:E20,"Ambos",'S4'!I6:I20)</f>
+        <f>SUMIF('S4'!E6:E22,"Víctor",'S4'!I6:I22)+SUMIF('S4'!E6:E22,"Ambos",'S4'!I6:I22)</f>
         <v/>
       </c>
       <c r="I8" s="7">
-        <f>SUMIF('S4'!E6:E20,"Diego",'S4'!I6:I20)+SUMIF('S4'!E6:E20,"Ambos",'S4'!I6:I20)</f>
+        <f>SUMIF('S4'!E6:E22,"Diego",'S4'!I6:I22)+SUMIF('S4'!E6:E22,"Ambos",'S4'!I6:I22)</f>
         <v/>
       </c>
       <c r="J8" s="7">
-        <f>COUNTIF('S4'!L6:L20,"&gt;0")</f>
+        <f>COUNTIF('S4'!L6:L22,"&gt;0")</f>
         <v/>
       </c>
     </row>
@@ -7085,10 +7087,12 @@
       <c r="I9" s="24" t="n">
         <v>1</v>
       </c>
-      <c r="J9" s="22" t="n"/>
+      <c r="J9" s="22" t="n">
+        <v>46314</v>
+      </c>
       <c r="K9" s="15" t="inlineStr">
         <is>
-          <t>En curso</t>
+          <t>Hecho</t>
         </is>
       </c>
       <c r="L9" s="15">
@@ -7102,7 +7106,7 @@
       </c>
       <c r="N9" s="15" t="inlineStr">
         <is>
-          <t>Diego acepta la invitación el 18-oct (vencía ese día)</t>
+          <t>Diego acepta la invitación el 18-oct (vencía ese día) · 19-oct: repo clonado y commit de prueba (00_Inbox/hola_diego.md)</t>
         </is>
       </c>
     </row>
@@ -7147,10 +7151,12 @@
       <c r="I10" s="24" t="n">
         <v>1</v>
       </c>
-      <c r="J10" s="22" t="n"/>
+      <c r="J10" s="22" t="n">
+        <v>46314</v>
+      </c>
       <c r="K10" s="15" t="inlineStr">
         <is>
-          <t>Movido</t>
+          <t>Hecho</t>
         </is>
       </c>
       <c r="L10" s="15">
@@ -7164,7 +7170,7 @@
       </c>
       <c r="N10" s="15" t="inlineStr">
         <is>
-          <t>Movido a la semana 19–24 oct (bloques dobles de Diego en IA_DIEGO.md)</t>
+          <t>Movido a la semana 19–24 oct (bloques dobles de Diego en IA_DIEGO.md) · 19-oct: RAG funcionando en la PC de Diego (586 notas indexadas)</t>
         </is>
       </c>
     </row>
@@ -7335,10 +7341,12 @@
       <c r="I13" s="24" t="n">
         <v>1.5</v>
       </c>
-      <c r="J13" s="22" t="n"/>
+      <c r="J13" s="22" t="n">
+        <v>46316</v>
+      </c>
       <c r="K13" s="15" t="inlineStr">
         <is>
-          <t>Movido</t>
+          <t>Hecho</t>
         </is>
       </c>
       <c r="L13" s="15">
@@ -7352,7 +7360,7 @@
       </c>
       <c r="N13" s="15" t="inlineStr">
         <is>
-          <t>Movido a la semana 19–24 oct (bloques dobles de Diego en IA_DIEGO.md)</t>
+          <t>Movido a la semana 19–24 oct (bloques dobles de Diego en IA_DIEGO.md) · 21-oct: 7 fichas verificadas de gestión del conocimiento (D01)</t>
         </is>
       </c>
     </row>
@@ -7397,10 +7405,12 @@
       <c r="I14" s="24" t="n">
         <v>0.5</v>
       </c>
-      <c r="J14" s="22" t="n"/>
+      <c r="J14" s="22" t="n">
+        <v>46314</v>
+      </c>
       <c r="K14" s="15" t="inlineStr">
         <is>
-          <t>Movido</t>
+          <t>Hecho</t>
         </is>
       </c>
       <c r="L14" s="15">
@@ -7414,7 +7424,7 @@
       </c>
       <c r="N14" s="15" t="inlineStr">
         <is>
-          <t>Movido a la semana 19–24 oct (bloques dobles de Diego en IA_DIEGO.md)</t>
+          <t>Movido a la semana 19–24 oct (bloques dobles de Diego en IA_DIEGO.md) · 19-oct: leído; 5 dudas en 00_Inbox/2026-10-19_reporte_Diego.md</t>
         </is>
       </c>
     </row>
@@ -7649,10 +7659,12 @@
       <c r="I18" s="24" t="n">
         <v>1.5</v>
       </c>
-      <c r="J18" s="22" t="n"/>
+      <c r="J18" s="22" t="n">
+        <v>46316</v>
+      </c>
       <c r="K18" s="15" t="inlineStr">
         <is>
-          <t>Movido</t>
+          <t>Hecho</t>
         </is>
       </c>
       <c r="L18" s="15">
@@ -7666,7 +7678,7 @@
       </c>
       <c r="N18" s="15" t="inlineStr">
         <is>
-          <t>Movido a la semana 19–24 oct (bloques dobles de Diego en IA_DIEGO.md)</t>
+          <t>Movido a la semana 19–24 oct (bloques dobles de Diego en IA_DIEGO.md) · 21-oct: 6 fichas verificadas de RAG (D02); A37 cubierta</t>
         </is>
       </c>
     </row>
@@ -7711,10 +7723,12 @@
       <c r="I19" s="24" t="n">
         <v>0.5</v>
       </c>
-      <c r="J19" s="22" t="n"/>
+      <c r="J19" s="22" t="n">
+        <v>46320</v>
+      </c>
       <c r="K19" s="15" t="inlineStr">
         <is>
-          <t>Movido</t>
+          <t>Hecho</t>
         </is>
       </c>
       <c r="L19" s="15">
@@ -7728,7 +7742,7 @@
       </c>
       <c r="N19" s="15" t="inlineStr">
         <is>
-          <t>Movido a la semana 19–24 oct (bloques dobles de Diego en IA_DIEGO.md)</t>
+          <t>Movido a la semana 19–24 oct (bloques dobles de Diego en IA_DIEGO.md) · 25-oct: 02_Fuentes/Tecnologia_IA/2026-10-25_Resumen_Bovedas_RAG.md</t>
         </is>
       </c>
     </row>
@@ -7852,7 +7866,7 @@
       </c>
       <c r="N21" s="15" t="inlineStr">
         <is>
-          <t>Movido: se aplica cuando Torvesa autorice (Diego consigue la información y los permisos)</t>
+          <t>Movido: se aplica cuando Torvesa autorice (Diego consigue la información y los permisos) · 27-oct: bloqueada, Torvesa aún no autoriza el campo; copia en S4-T16 (reprogramada 27-oct)</t>
         </is>
       </c>
     </row>
@@ -7976,7 +7990,7 @@
       </c>
       <c r="N23" s="15" t="inlineStr">
         <is>
-          <t>Movido: se aplica cuando Torvesa autorice (Diego consigue la información y los permisos)</t>
+          <t>Movido: se aplica cuando Torvesa autorice (Diego consigue la información y los permisos) · 27-oct: bloqueada, Torvesa aún no autoriza el campo; copia en S4-T16 (reprogramada 27-oct)</t>
         </is>
       </c>
     </row>
@@ -8211,10 +8225,12 @@
       <c r="I27" s="24" t="n">
         <v>1.5</v>
       </c>
-      <c r="J27" s="22" t="n"/>
+      <c r="J27" s="22" t="n">
+        <v>46320</v>
+      </c>
       <c r="K27" s="15" t="inlineStr">
         <is>
-          <t>Movido</t>
+          <t>Hecho</t>
         </is>
       </c>
       <c r="L27" s="15">
@@ -8228,7 +8244,7 @@
       </c>
       <c r="N27" s="15" t="inlineStr">
         <is>
-          <t>Movido a la semana 19–24 oct (bloques dobles de Diego en IA_DIEGO.md)</t>
+          <t>Movido a la semana 19–24 oct (bloques dobles de Diego en IA_DIEGO.md) · 25-oct: 6 fichas verificadas de BPMN y procesos, incluida la especificación OMG</t>
         </is>
       </c>
     </row>
@@ -8273,10 +8289,12 @@
       <c r="I28" s="24" t="n">
         <v>2</v>
       </c>
-      <c r="J28" s="22" t="n"/>
+      <c r="J28" s="22" t="n">
+        <v>46320</v>
+      </c>
       <c r="K28" s="15" t="inlineStr">
         <is>
-          <t>Movido</t>
+          <t>Hecho</t>
         </is>
       </c>
       <c r="L28" s="15">
@@ -8290,7 +8308,7 @@
       </c>
       <c r="N28" s="15" t="inlineStr">
         <is>
-          <t>Movido a la semana 19–24 oct (bloques dobles de Diego en IA_DIEGO.md)</t>
+          <t>Movido a la semana 19–24 oct (bloques dobles de Diego en IA_DIEGO.md) · 25-oct: fichas de precios de CRM, mensajería, bóveda y LLM (bloques G y H)</t>
         </is>
       </c>
     </row>
@@ -8352,7 +8370,7 @@
       </c>
       <c r="N29" s="15" t="inlineStr">
         <is>
-          <t>Movido: se aplica cuando Torvesa autorice (Diego consigue la información y los permisos). Al día siguiente del campo</t>
+          <t>Movido: se aplica cuando Torvesa autorice (Diego consigue la información y los permisos). Al día siguiente del campo · 27-oct: bloqueada, sin datos de campo; se hace al día siguiente del campo (S4-T16)</t>
         </is>
       </c>
     </row>
@@ -8461,10 +8479,12 @@
       <c r="I31" s="24" t="n">
         <v>0.5</v>
       </c>
-      <c r="J31" s="22" t="n"/>
+      <c r="J31" s="22" t="n">
+        <v>46320</v>
+      </c>
       <c r="K31" s="15" t="inlineStr">
         <is>
-          <t>Movido</t>
+          <t>Hecho</t>
         </is>
       </c>
       <c r="L31" s="15">
@@ -8478,7 +8498,7 @@
       </c>
       <c r="N31" s="15" t="inlineStr">
         <is>
-          <t>Movido a la semana 19–24 oct (bloques dobles de Diego en IA_DIEGO.md)</t>
+          <t>Movido a la semana 19–24 oct (bloques dobles de Diego en IA_DIEGO.md) · 25-oct: 02_Fuentes/Casos_Estudio/2026-10-25_Resumen_CRM_Flujos.md</t>
         </is>
       </c>
     </row>
@@ -8630,6 +8650,7 @@
       <c r="M2" s="2" t="n"/>
       <c r="N2" s="2" t="n"/>
     </row>
+    <row r="3"/>
     <row r="4">
       <c r="A4" s="6" t="inlineStr">
         <is>
@@ -8680,19 +8701,19 @@
         <v/>
       </c>
       <c r="D5" s="21">
-        <f>SUMIFS('S1'!$I$6:$I$32,'S1'!$B$6:$B$32,$A5,'S1'!$E$6:$E$32,"Víctor")+SUMIFS('S1'!$I$6:$I$32,'S1'!$B$6:$B$32,$A5,'S1'!$E$6:$E$32,"Ambos")+SUMIFS('S2'!$I$6:$I$23,'S2'!$B$6:$B$23,$A5,'S2'!$E$6:$E$23,"Víctor")+SUMIFS('S2'!$I$6:$I$23,'S2'!$B$6:$B$23,$A5,'S2'!$E$6:$E$23,"Ambos")+SUMIFS('S3'!$I$6:$I$19,'S3'!$B$6:$B$19,$A5,'S3'!$E$6:$E$19,"Víctor")+SUMIFS('S3'!$I$6:$I$19,'S3'!$B$6:$B$19,$A5,'S3'!$E$6:$E$19,"Ambos")+SUMIFS('S4'!$I$6:$I$20,'S4'!$B$6:$B$20,$A5,'S4'!$E$6:$E$20,"Víctor")+SUMIFS('S4'!$I$6:$I$20,'S4'!$B$6:$B$20,$A5,'S4'!$E$6:$E$20,"Ambos")+SUMIFS('S5'!$I$6:$I$20,'S5'!$B$6:$B$20,$A5,'S5'!$E$6:$E$20,"Víctor")+SUMIFS('S5'!$I$6:$I$20,'S5'!$B$6:$B$20,$A5,'S5'!$E$6:$E$20,"Ambos")+SUMIFS('S6'!$I$6:$I$17,'S6'!$B$6:$B$17,$A5,'S6'!$E$6:$E$17,"Víctor")+SUMIFS('S6'!$I$6:$I$17,'S6'!$B$6:$B$17,$A5,'S6'!$E$6:$E$17,"Ambos")+SUMIFS('S7'!$I$6:$I$19,'S7'!$B$6:$B$19,$A5,'S7'!$E$6:$E$19,"Víctor")+SUMIFS('S7'!$I$6:$I$19,'S7'!$B$6:$B$19,$A5,'S7'!$E$6:$E$19,"Ambos")+SUMIFS('S8'!$I$6:$I$23,'S8'!$B$6:$B$23,$A5,'S8'!$E$6:$E$23,"Víctor")+SUMIFS('S8'!$I$6:$I$23,'S8'!$B$6:$B$23,$A5,'S8'!$E$6:$E$23,"Ambos")+SUMIFS('S9'!$I$6:$I$15,'S9'!$B$6:$B$15,$A5,'S9'!$E$6:$E$15,"Víctor")+SUMIFS('S9'!$I$6:$I$15,'S9'!$B$6:$B$15,$A5,'S9'!$E$6:$E$15,"Ambos")+SUMIFS('S10'!$I$6:$I$13,'S10'!$B$6:$B$13,$A5,'S10'!$E$6:$E$13,"Víctor")+SUMIFS('S10'!$I$6:$I$13,'S10'!$B$6:$B$13,$A5,'S10'!$E$6:$E$13,"Ambos")+SUMIFS('Holgura'!$I$6:$I$11,'Holgura'!$B$6:$B$11,$A5,'Holgura'!$E$6:$E$11,"Víctor")+SUMIFS('Holgura'!$I$6:$I$11,'Holgura'!$B$6:$B$11,$A5,'Holgura'!$E$6:$E$11,"Ambos")+SUMIFS('Entrega'!$I$6:$I$9,'Entrega'!$B$6:$B$9,$A5,'Entrega'!$E$6:$E$9,"Víctor")+SUMIFS('Entrega'!$I$6:$I$9,'Entrega'!$B$6:$B$9,$A5,'Entrega'!$E$6:$E$9,"Ambos")+SUMIFS('Defensa'!$I$6:$I$10,'Defensa'!$B$6:$B$10,$A5,'Defensa'!$E$6:$E$10,"Víctor")+SUMIFS('Defensa'!$I$6:$I$10,'Defensa'!$B$6:$B$10,$A5,'Defensa'!$E$6:$E$10,"Ambos")</f>
+        <f>SUMIFS('S1'!$I$6:$I$32,'S1'!$B$6:$B$32,$A5,'S1'!$E$6:$E$32,"Víctor")+SUMIFS('S1'!$I$6:$I$32,'S1'!$B$6:$B$32,$A5,'S1'!$E$6:$E$32,"Ambos")+SUMIFS('S2'!$I$6:$I$23,'S2'!$B$6:$B$23,$A5,'S2'!$E$6:$E$23,"Víctor")+SUMIFS('S2'!$I$6:$I$23,'S2'!$B$6:$B$23,$A5,'S2'!$E$6:$E$23,"Ambos")+SUMIFS('S3'!$I$6:$I$24,'S3'!$B$6:$B$24,$A5,'S3'!$E$6:$E$24,"Víctor")+SUMIFS('S3'!$I$6:$I$24,'S3'!$B$6:$B$24,$A5,'S3'!$E$6:$E$24,"Ambos")+SUMIFS('S4'!$I$6:$I$22,'S4'!$B$6:$B$22,$A5,'S4'!$E$6:$E$22,"Víctor")+SUMIFS('S4'!$I$6:$I$22,'S4'!$B$6:$B$22,$A5,'S4'!$E$6:$E$22,"Ambos")+SUMIFS('S5'!$I$6:$I$20,'S5'!$B$6:$B$20,$A5,'S5'!$E$6:$E$20,"Víctor")+SUMIFS('S5'!$I$6:$I$20,'S5'!$B$6:$B$20,$A5,'S5'!$E$6:$E$20,"Ambos")+SUMIFS('S6'!$I$6:$I$17,'S6'!$B$6:$B$17,$A5,'S6'!$E$6:$E$17,"Víctor")+SUMIFS('S6'!$I$6:$I$17,'S6'!$B$6:$B$17,$A5,'S6'!$E$6:$E$17,"Ambos")+SUMIFS('S7'!$I$6:$I$19,'S7'!$B$6:$B$19,$A5,'S7'!$E$6:$E$19,"Víctor")+SUMIFS('S7'!$I$6:$I$19,'S7'!$B$6:$B$19,$A5,'S7'!$E$6:$E$19,"Ambos")+SUMIFS('S8'!$I$6:$I$23,'S8'!$B$6:$B$23,$A5,'S8'!$E$6:$E$23,"Víctor")+SUMIFS('S8'!$I$6:$I$23,'S8'!$B$6:$B$23,$A5,'S8'!$E$6:$E$23,"Ambos")+SUMIFS('S9'!$I$6:$I$15,'S9'!$B$6:$B$15,$A5,'S9'!$E$6:$E$15,"Víctor")+SUMIFS('S9'!$I$6:$I$15,'S9'!$B$6:$B$15,$A5,'S9'!$E$6:$E$15,"Ambos")+SUMIFS('S10'!$I$6:$I$13,'S10'!$B$6:$B$13,$A5,'S10'!$E$6:$E$13,"Víctor")+SUMIFS('S10'!$I$6:$I$13,'S10'!$B$6:$B$13,$A5,'S10'!$E$6:$E$13,"Ambos")+SUMIFS('Holgura'!$I$6:$I$11,'Holgura'!$B$6:$B$11,$A5,'Holgura'!$E$6:$E$11,"Víctor")+SUMIFS('Holgura'!$I$6:$I$11,'Holgura'!$B$6:$B$11,$A5,'Holgura'!$E$6:$E$11,"Ambos")+SUMIFS('Entrega'!$I$6:$I$9,'Entrega'!$B$6:$B$9,$A5,'Entrega'!$E$6:$E$9,"Víctor")+SUMIFS('Entrega'!$I$6:$I$9,'Entrega'!$B$6:$B$9,$A5,'Entrega'!$E$6:$E$9,"Ambos")+SUMIFS('Defensa'!$I$6:$I$10,'Defensa'!$B$6:$B$10,$A5,'Defensa'!$E$6:$E$10,"Víctor")+SUMIFS('Defensa'!$I$6:$I$10,'Defensa'!$B$6:$B$10,$A5,'Defensa'!$E$6:$E$10,"Ambos")</f>
         <v/>
       </c>
       <c r="E5" s="21">
-        <f>SUMIFS('S1'!$I$6:$I$32,'S1'!$B$6:$B$32,$A5,'S1'!$E$6:$E$32,"Diego")+SUMIFS('S1'!$I$6:$I$32,'S1'!$B$6:$B$32,$A5,'S1'!$E$6:$E$32,"Ambos")+SUMIFS('S2'!$I$6:$I$23,'S2'!$B$6:$B$23,$A5,'S2'!$E$6:$E$23,"Diego")+SUMIFS('S2'!$I$6:$I$23,'S2'!$B$6:$B$23,$A5,'S2'!$E$6:$E$23,"Ambos")+SUMIFS('S3'!$I$6:$I$19,'S3'!$B$6:$B$19,$A5,'S3'!$E$6:$E$19,"Diego")+SUMIFS('S3'!$I$6:$I$19,'S3'!$B$6:$B$19,$A5,'S3'!$E$6:$E$19,"Ambos")+SUMIFS('S4'!$I$6:$I$20,'S4'!$B$6:$B$20,$A5,'S4'!$E$6:$E$20,"Diego")+SUMIFS('S4'!$I$6:$I$20,'S4'!$B$6:$B$20,$A5,'S4'!$E$6:$E$20,"Ambos")+SUMIFS('S5'!$I$6:$I$20,'S5'!$B$6:$B$20,$A5,'S5'!$E$6:$E$20,"Diego")+SUMIFS('S5'!$I$6:$I$20,'S5'!$B$6:$B$20,$A5,'S5'!$E$6:$E$20,"Ambos")+SUMIFS('S6'!$I$6:$I$17,'S6'!$B$6:$B$17,$A5,'S6'!$E$6:$E$17,"Diego")+SUMIFS('S6'!$I$6:$I$17,'S6'!$B$6:$B$17,$A5,'S6'!$E$6:$E$17,"Ambos")+SUMIFS('S7'!$I$6:$I$19,'S7'!$B$6:$B$19,$A5,'S7'!$E$6:$E$19,"Diego")+SUMIFS('S7'!$I$6:$I$19,'S7'!$B$6:$B$19,$A5,'S7'!$E$6:$E$19,"Ambos")+SUMIFS('S8'!$I$6:$I$23,'S8'!$B$6:$B$23,$A5,'S8'!$E$6:$E$23,"Diego")+SUMIFS('S8'!$I$6:$I$23,'S8'!$B$6:$B$23,$A5,'S8'!$E$6:$E$23,"Ambos")+SUMIFS('S9'!$I$6:$I$15,'S9'!$B$6:$B$15,$A5,'S9'!$E$6:$E$15,"Diego")+SUMIFS('S9'!$I$6:$I$15,'S9'!$B$6:$B$15,$A5,'S9'!$E$6:$E$15,"Ambos")+SUMIFS('S10'!$I$6:$I$13,'S10'!$B$6:$B$13,$A5,'S10'!$E$6:$E$13,"Diego")+SUMIFS('S10'!$I$6:$I$13,'S10'!$B$6:$B$13,$A5,'S10'!$E$6:$E$13,"Ambos")+SUMIFS('Holgura'!$I$6:$I$11,'Holgura'!$B$6:$B$11,$A5,'Holgura'!$E$6:$E$11,"Diego")+SUMIFS('Holgura'!$I$6:$I$11,'Holgura'!$B$6:$B$11,$A5,'Holgura'!$E$6:$E$11,"Ambos")+SUMIFS('Entrega'!$I$6:$I$9,'Entrega'!$B$6:$B$9,$A5,'Entrega'!$E$6:$E$9,"Diego")+SUMIFS('Entrega'!$I$6:$I$9,'Entrega'!$B$6:$B$9,$A5,'Entrega'!$E$6:$E$9,"Ambos")+SUMIFS('Defensa'!$I$6:$I$10,'Defensa'!$B$6:$B$10,$A5,'Defensa'!$E$6:$E$10,"Diego")+SUMIFS('Defensa'!$I$6:$I$10,'Defensa'!$B$6:$B$10,$A5,'Defensa'!$E$6:$E$10,"Ambos")</f>
+        <f>SUMIFS('S1'!$I$6:$I$32,'S1'!$B$6:$B$32,$A5,'S1'!$E$6:$E$32,"Diego")+SUMIFS('S1'!$I$6:$I$32,'S1'!$B$6:$B$32,$A5,'S1'!$E$6:$E$32,"Ambos")+SUMIFS('S2'!$I$6:$I$23,'S2'!$B$6:$B$23,$A5,'S2'!$E$6:$E$23,"Diego")+SUMIFS('S2'!$I$6:$I$23,'S2'!$B$6:$B$23,$A5,'S2'!$E$6:$E$23,"Ambos")+SUMIFS('S3'!$I$6:$I$24,'S3'!$B$6:$B$24,$A5,'S3'!$E$6:$E$24,"Diego")+SUMIFS('S3'!$I$6:$I$24,'S3'!$B$6:$B$24,$A5,'S3'!$E$6:$E$24,"Ambos")+SUMIFS('S4'!$I$6:$I$22,'S4'!$B$6:$B$22,$A5,'S4'!$E$6:$E$22,"Diego")+SUMIFS('S4'!$I$6:$I$22,'S4'!$B$6:$B$22,$A5,'S4'!$E$6:$E$22,"Ambos")+SUMIFS('S5'!$I$6:$I$20,'S5'!$B$6:$B$20,$A5,'S5'!$E$6:$E$20,"Diego")+SUMIFS('S5'!$I$6:$I$20,'S5'!$B$6:$B$20,$A5,'S5'!$E$6:$E$20,"Ambos")+SUMIFS('S6'!$I$6:$I$17,'S6'!$B$6:$B$17,$A5,'S6'!$E$6:$E$17,"Diego")+SUMIFS('S6'!$I$6:$I$17,'S6'!$B$6:$B$17,$A5,'S6'!$E$6:$E$17,"Ambos")+SUMIFS('S7'!$I$6:$I$19,'S7'!$B$6:$B$19,$A5,'S7'!$E$6:$E$19,"Diego")+SUMIFS('S7'!$I$6:$I$19,'S7'!$B$6:$B$19,$A5,'S7'!$E$6:$E$19,"Ambos")+SUMIFS('S8'!$I$6:$I$23,'S8'!$B$6:$B$23,$A5,'S8'!$E$6:$E$23,"Diego")+SUMIFS('S8'!$I$6:$I$23,'S8'!$B$6:$B$23,$A5,'S8'!$E$6:$E$23,"Ambos")+SUMIFS('S9'!$I$6:$I$15,'S9'!$B$6:$B$15,$A5,'S9'!$E$6:$E$15,"Diego")+SUMIFS('S9'!$I$6:$I$15,'S9'!$B$6:$B$15,$A5,'S9'!$E$6:$E$15,"Ambos")+SUMIFS('S10'!$I$6:$I$13,'S10'!$B$6:$B$13,$A5,'S10'!$E$6:$E$13,"Diego")+SUMIFS('S10'!$I$6:$I$13,'S10'!$B$6:$B$13,$A5,'S10'!$E$6:$E$13,"Ambos")+SUMIFS('Holgura'!$I$6:$I$11,'Holgura'!$B$6:$B$11,$A5,'Holgura'!$E$6:$E$11,"Diego")+SUMIFS('Holgura'!$I$6:$I$11,'Holgura'!$B$6:$B$11,$A5,'Holgura'!$E$6:$E$11,"Ambos")+SUMIFS('Entrega'!$I$6:$I$9,'Entrega'!$B$6:$B$9,$A5,'Entrega'!$E$6:$E$9,"Diego")+SUMIFS('Entrega'!$I$6:$I$9,'Entrega'!$B$6:$B$9,$A5,'Entrega'!$E$6:$E$9,"Ambos")+SUMIFS('Defensa'!$I$6:$I$10,'Defensa'!$B$6:$B$10,$A5,'Defensa'!$E$6:$E$10,"Diego")+SUMIFS('Defensa'!$I$6:$I$10,'Defensa'!$B$6:$B$10,$A5,'Defensa'!$E$6:$E$10,"Ambos")</f>
         <v/>
       </c>
       <c r="F5" s="21">
-        <f>COUNTIFS('S1'!$B$6:$B$32,$A5,'S1'!$E$6:$E$32,"Víctor")+COUNTIFS('S1'!$B$6:$B$32,$A5,'S1'!$E$6:$E$32,"Ambos")+COUNTIFS('S2'!$B$6:$B$23,$A5,'S2'!$E$6:$E$23,"Víctor")+COUNTIFS('S2'!$B$6:$B$23,$A5,'S2'!$E$6:$E$23,"Ambos")+COUNTIFS('S3'!$B$6:$B$19,$A5,'S3'!$E$6:$E$19,"Víctor")+COUNTIFS('S3'!$B$6:$B$19,$A5,'S3'!$E$6:$E$19,"Ambos")+COUNTIFS('S4'!$B$6:$B$20,$A5,'S4'!$E$6:$E$20,"Víctor")+COUNTIFS('S4'!$B$6:$B$20,$A5,'S4'!$E$6:$E$20,"Ambos")+COUNTIFS('S5'!$B$6:$B$20,$A5,'S5'!$E$6:$E$20,"Víctor")+COUNTIFS('S5'!$B$6:$B$20,$A5,'S5'!$E$6:$E$20,"Ambos")+COUNTIFS('S6'!$B$6:$B$17,$A5,'S6'!$E$6:$E$17,"Víctor")+COUNTIFS('S6'!$B$6:$B$17,$A5,'S6'!$E$6:$E$17,"Ambos")+COUNTIFS('S7'!$B$6:$B$19,$A5,'S7'!$E$6:$E$19,"Víctor")+COUNTIFS('S7'!$B$6:$B$19,$A5,'S7'!$E$6:$E$19,"Ambos")+COUNTIFS('S8'!$B$6:$B$23,$A5,'S8'!$E$6:$E$23,"Víctor")+COUNTIFS('S8'!$B$6:$B$23,$A5,'S8'!$E$6:$E$23,"Ambos")+COUNTIFS('S9'!$B$6:$B$15,$A5,'S9'!$E$6:$E$15,"Víctor")+COUNTIFS('S9'!$B$6:$B$15,$A5,'S9'!$E$6:$E$15,"Ambos")+COUNTIFS('S10'!$B$6:$B$13,$A5,'S10'!$E$6:$E$13,"Víctor")+COUNTIFS('S10'!$B$6:$B$13,$A5,'S10'!$E$6:$E$13,"Ambos")+COUNTIFS('Holgura'!$B$6:$B$11,$A5,'Holgura'!$E$6:$E$11,"Víctor")+COUNTIFS('Holgura'!$B$6:$B$11,$A5,'Holgura'!$E$6:$E$11,"Ambos")+COUNTIFS('Entrega'!$B$6:$B$9,$A5,'Entrega'!$E$6:$E$9,"Víctor")+COUNTIFS('Entrega'!$B$6:$B$9,$A5,'Entrega'!$E$6:$E$9,"Ambos")+COUNTIFS('Defensa'!$B$6:$B$10,$A5,'Defensa'!$E$6:$E$10,"Víctor")+COUNTIFS('Defensa'!$B$6:$B$10,$A5,'Defensa'!$E$6:$E$10,"Ambos")</f>
+        <f>COUNTIFS('S1'!$B$6:$B$32,$A5,'S1'!$E$6:$E$32,"Víctor")+COUNTIFS('S1'!$B$6:$B$32,$A5,'S1'!$E$6:$E$32,"Ambos")+COUNTIFS('S2'!$B$6:$B$23,$A5,'S2'!$E$6:$E$23,"Víctor")+COUNTIFS('S2'!$B$6:$B$23,$A5,'S2'!$E$6:$E$23,"Ambos")+COUNTIFS('S3'!$B$6:$B$24,$A5,'S3'!$E$6:$E$24,"Víctor")+COUNTIFS('S3'!$B$6:$B$24,$A5,'S3'!$E$6:$E$24,"Ambos")+COUNTIFS('S4'!$B$6:$B$22,$A5,'S4'!$E$6:$E$22,"Víctor")+COUNTIFS('S4'!$B$6:$B$22,$A5,'S4'!$E$6:$E$22,"Ambos")+COUNTIFS('S5'!$B$6:$B$20,$A5,'S5'!$E$6:$E$20,"Víctor")+COUNTIFS('S5'!$B$6:$B$20,$A5,'S5'!$E$6:$E$20,"Ambos")+COUNTIFS('S6'!$B$6:$B$17,$A5,'S6'!$E$6:$E$17,"Víctor")+COUNTIFS('S6'!$B$6:$B$17,$A5,'S6'!$E$6:$E$17,"Ambos")+COUNTIFS('S7'!$B$6:$B$19,$A5,'S7'!$E$6:$E$19,"Víctor")+COUNTIFS('S7'!$B$6:$B$19,$A5,'S7'!$E$6:$E$19,"Ambos")+COUNTIFS('S8'!$B$6:$B$23,$A5,'S8'!$E$6:$E$23,"Víctor")+COUNTIFS('S8'!$B$6:$B$23,$A5,'S8'!$E$6:$E$23,"Ambos")+COUNTIFS('S9'!$B$6:$B$15,$A5,'S9'!$E$6:$E$15,"Víctor")+COUNTIFS('S9'!$B$6:$B$15,$A5,'S9'!$E$6:$E$15,"Ambos")+COUNTIFS('S10'!$B$6:$B$13,$A5,'S10'!$E$6:$E$13,"Víctor")+COUNTIFS('S10'!$B$6:$B$13,$A5,'S10'!$E$6:$E$13,"Ambos")+COUNTIFS('Holgura'!$B$6:$B$11,$A5,'Holgura'!$E$6:$E$11,"Víctor")+COUNTIFS('Holgura'!$B$6:$B$11,$A5,'Holgura'!$E$6:$E$11,"Ambos")+COUNTIFS('Entrega'!$B$6:$B$9,$A5,'Entrega'!$E$6:$E$9,"Víctor")+COUNTIFS('Entrega'!$B$6:$B$9,$A5,'Entrega'!$E$6:$E$9,"Ambos")+COUNTIFS('Defensa'!$B$6:$B$10,$A5,'Defensa'!$E$6:$E$10,"Víctor")+COUNTIFS('Defensa'!$B$6:$B$10,$A5,'Defensa'!$E$6:$E$10,"Ambos")</f>
         <v/>
       </c>
       <c r="G5" s="21">
-        <f>COUNTIFS('S1'!$B$6:$B$32,$A5,'S1'!$E$6:$E$32,"Diego")+COUNTIFS('S1'!$B$6:$B$32,$A5,'S1'!$E$6:$E$32,"Ambos")+COUNTIFS('S2'!$B$6:$B$23,$A5,'S2'!$E$6:$E$23,"Diego")+COUNTIFS('S2'!$B$6:$B$23,$A5,'S2'!$E$6:$E$23,"Ambos")+COUNTIFS('S3'!$B$6:$B$19,$A5,'S3'!$E$6:$E$19,"Diego")+COUNTIFS('S3'!$B$6:$B$19,$A5,'S3'!$E$6:$E$19,"Ambos")+COUNTIFS('S4'!$B$6:$B$20,$A5,'S4'!$E$6:$E$20,"Diego")+COUNTIFS('S4'!$B$6:$B$20,$A5,'S4'!$E$6:$E$20,"Ambos")+COUNTIFS('S5'!$B$6:$B$20,$A5,'S5'!$E$6:$E$20,"Diego")+COUNTIFS('S5'!$B$6:$B$20,$A5,'S5'!$E$6:$E$20,"Ambos")+COUNTIFS('S6'!$B$6:$B$17,$A5,'S6'!$E$6:$E$17,"Diego")+COUNTIFS('S6'!$B$6:$B$17,$A5,'S6'!$E$6:$E$17,"Ambos")+COUNTIFS('S7'!$B$6:$B$19,$A5,'S7'!$E$6:$E$19,"Diego")+COUNTIFS('S7'!$B$6:$B$19,$A5,'S7'!$E$6:$E$19,"Ambos")+COUNTIFS('S8'!$B$6:$B$23,$A5,'S8'!$E$6:$E$23,"Diego")+COUNTIFS('S8'!$B$6:$B$23,$A5,'S8'!$E$6:$E$23,"Ambos")+COUNTIFS('S9'!$B$6:$B$15,$A5,'S9'!$E$6:$E$15,"Diego")+COUNTIFS('S9'!$B$6:$B$15,$A5,'S9'!$E$6:$E$15,"Ambos")+COUNTIFS('S10'!$B$6:$B$13,$A5,'S10'!$E$6:$E$13,"Diego")+COUNTIFS('S10'!$B$6:$B$13,$A5,'S10'!$E$6:$E$13,"Ambos")+COUNTIFS('Holgura'!$B$6:$B$11,$A5,'Holgura'!$E$6:$E$11,"Diego")+COUNTIFS('Holgura'!$B$6:$B$11,$A5,'Holgura'!$E$6:$E$11,"Ambos")+COUNTIFS('Entrega'!$B$6:$B$9,$A5,'Entrega'!$E$6:$E$9,"Diego")+COUNTIFS('Entrega'!$B$6:$B$9,$A5,'Entrega'!$E$6:$E$9,"Ambos")+COUNTIFS('Defensa'!$B$6:$B$10,$A5,'Defensa'!$E$6:$E$10,"Diego")+COUNTIFS('Defensa'!$B$6:$B$10,$A5,'Defensa'!$E$6:$E$10,"Ambos")</f>
+        <f>COUNTIFS('S1'!$B$6:$B$32,$A5,'S1'!$E$6:$E$32,"Diego")+COUNTIFS('S1'!$B$6:$B$32,$A5,'S1'!$E$6:$E$32,"Ambos")+COUNTIFS('S2'!$B$6:$B$23,$A5,'S2'!$E$6:$E$23,"Diego")+COUNTIFS('S2'!$B$6:$B$23,$A5,'S2'!$E$6:$E$23,"Ambos")+COUNTIFS('S3'!$B$6:$B$24,$A5,'S3'!$E$6:$E$24,"Diego")+COUNTIFS('S3'!$B$6:$B$24,$A5,'S3'!$E$6:$E$24,"Ambos")+COUNTIFS('S4'!$B$6:$B$22,$A5,'S4'!$E$6:$E$22,"Diego")+COUNTIFS('S4'!$B$6:$B$22,$A5,'S4'!$E$6:$E$22,"Ambos")+COUNTIFS('S5'!$B$6:$B$20,$A5,'S5'!$E$6:$E$20,"Diego")+COUNTIFS('S5'!$B$6:$B$20,$A5,'S5'!$E$6:$E$20,"Ambos")+COUNTIFS('S6'!$B$6:$B$17,$A5,'S6'!$E$6:$E$17,"Diego")+COUNTIFS('S6'!$B$6:$B$17,$A5,'S6'!$E$6:$E$17,"Ambos")+COUNTIFS('S7'!$B$6:$B$19,$A5,'S7'!$E$6:$E$19,"Diego")+COUNTIFS('S7'!$B$6:$B$19,$A5,'S7'!$E$6:$E$19,"Ambos")+COUNTIFS('S8'!$B$6:$B$23,$A5,'S8'!$E$6:$E$23,"Diego")+COUNTIFS('S8'!$B$6:$B$23,$A5,'S8'!$E$6:$E$23,"Ambos")+COUNTIFS('S9'!$B$6:$B$15,$A5,'S9'!$E$6:$E$15,"Diego")+COUNTIFS('S9'!$B$6:$B$15,$A5,'S9'!$E$6:$E$15,"Ambos")+COUNTIFS('S10'!$B$6:$B$13,$A5,'S10'!$E$6:$E$13,"Diego")+COUNTIFS('S10'!$B$6:$B$13,$A5,'S10'!$E$6:$E$13,"Ambos")+COUNTIFS('Holgura'!$B$6:$B$11,$A5,'Holgura'!$E$6:$E$11,"Diego")+COUNTIFS('Holgura'!$B$6:$B$11,$A5,'Holgura'!$E$6:$E$11,"Ambos")+COUNTIFS('Entrega'!$B$6:$B$9,$A5,'Entrega'!$E$6:$E$9,"Diego")+COUNTIFS('Entrega'!$B$6:$B$9,$A5,'Entrega'!$E$6:$E$9,"Ambos")+COUNTIFS('Defensa'!$B$6:$B$10,$A5,'Defensa'!$E$6:$E$10,"Diego")+COUNTIFS('Defensa'!$B$6:$B$10,$A5,'Defensa'!$E$6:$E$10,"Ambos")</f>
         <v/>
       </c>
     </row>
@@ -8709,19 +8730,19 @@
         <v/>
       </c>
       <c r="D6" s="21">
-        <f>SUMIFS('S1'!$I$6:$I$32,'S1'!$B$6:$B$32,$A6,'S1'!$E$6:$E$32,"Víctor")+SUMIFS('S1'!$I$6:$I$32,'S1'!$B$6:$B$32,$A6,'S1'!$E$6:$E$32,"Ambos")+SUMIFS('S2'!$I$6:$I$23,'S2'!$B$6:$B$23,$A6,'S2'!$E$6:$E$23,"Víctor")+SUMIFS('S2'!$I$6:$I$23,'S2'!$B$6:$B$23,$A6,'S2'!$E$6:$E$23,"Ambos")+SUMIFS('S3'!$I$6:$I$19,'S3'!$B$6:$B$19,$A6,'S3'!$E$6:$E$19,"Víctor")+SUMIFS('S3'!$I$6:$I$19,'S3'!$B$6:$B$19,$A6,'S3'!$E$6:$E$19,"Ambos")+SUMIFS('S4'!$I$6:$I$20,'S4'!$B$6:$B$20,$A6,'S4'!$E$6:$E$20,"Víctor")+SUMIFS('S4'!$I$6:$I$20,'S4'!$B$6:$B$20,$A6,'S4'!$E$6:$E$20,"Ambos")+SUMIFS('S5'!$I$6:$I$20,'S5'!$B$6:$B$20,$A6,'S5'!$E$6:$E$20,"Víctor")+SUMIFS('S5'!$I$6:$I$20,'S5'!$B$6:$B$20,$A6,'S5'!$E$6:$E$20,"Ambos")+SUMIFS('S6'!$I$6:$I$17,'S6'!$B$6:$B$17,$A6,'S6'!$E$6:$E$17,"Víctor")+SUMIFS('S6'!$I$6:$I$17,'S6'!$B$6:$B$17,$A6,'S6'!$E$6:$E$17,"Ambos")+SUMIFS('S7'!$I$6:$I$19,'S7'!$B$6:$B$19,$A6,'S7'!$E$6:$E$19,"Víctor")+SUMIFS('S7'!$I$6:$I$19,'S7'!$B$6:$B$19,$A6,'S7'!$E$6:$E$19,"Ambos")+SUMIFS('S8'!$I$6:$I$23,'S8'!$B$6:$B$23,$A6,'S8'!$E$6:$E$23,"Víctor")+SUMIFS('S8'!$I$6:$I$23,'S8'!$B$6:$B$23,$A6,'S8'!$E$6:$E$23,"Ambos")+SUMIFS('S9'!$I$6:$I$15,'S9'!$B$6:$B$15,$A6,'S9'!$E$6:$E$15,"Víctor")+SUMIFS('S9'!$I$6:$I$15,'S9'!$B$6:$B$15,$A6,'S9'!$E$6:$E$15,"Ambos")+SUMIFS('S10'!$I$6:$I$13,'S10'!$B$6:$B$13,$A6,'S10'!$E$6:$E$13,"Víctor")+SUMIFS('S10'!$I$6:$I$13,'S10'!$B$6:$B$13,$A6,'S10'!$E$6:$E$13,"Ambos")+SUMIFS('Holgura'!$I$6:$I$11,'Holgura'!$B$6:$B$11,$A6,'Holgura'!$E$6:$E$11,"Víctor")+SUMIFS('Holgura'!$I$6:$I$11,'Holgura'!$B$6:$B$11,$A6,'Holgura'!$E$6:$E$11,"Ambos")+SUMIFS('Entrega'!$I$6:$I$9,'Entrega'!$B$6:$B$9,$A6,'Entrega'!$E$6:$E$9,"Víctor")+SUMIFS('Entrega'!$I$6:$I$9,'Entrega'!$B$6:$B$9,$A6,'Entrega'!$E$6:$E$9,"Ambos")+SUMIFS('Defensa'!$I$6:$I$10,'Defensa'!$B$6:$B$10,$A6,'Defensa'!$E$6:$E$10,"Víctor")+SUMIFS('Defensa'!$I$6:$I$10,'Defensa'!$B$6:$B$10,$A6,'Defensa'!$E$6:$E$10,"Ambos")</f>
+        <f>SUMIFS('S1'!$I$6:$I$32,'S1'!$B$6:$B$32,$A6,'S1'!$E$6:$E$32,"Víctor")+SUMIFS('S1'!$I$6:$I$32,'S1'!$B$6:$B$32,$A6,'S1'!$E$6:$E$32,"Ambos")+SUMIFS('S2'!$I$6:$I$23,'S2'!$B$6:$B$23,$A6,'S2'!$E$6:$E$23,"Víctor")+SUMIFS('S2'!$I$6:$I$23,'S2'!$B$6:$B$23,$A6,'S2'!$E$6:$E$23,"Ambos")+SUMIFS('S3'!$I$6:$I$24,'S3'!$B$6:$B$24,$A6,'S3'!$E$6:$E$24,"Víctor")+SUMIFS('S3'!$I$6:$I$24,'S3'!$B$6:$B$24,$A6,'S3'!$E$6:$E$24,"Ambos")+SUMIFS('S4'!$I$6:$I$22,'S4'!$B$6:$B$22,$A6,'S4'!$E$6:$E$22,"Víctor")+SUMIFS('S4'!$I$6:$I$22,'S4'!$B$6:$B$22,$A6,'S4'!$E$6:$E$22,"Ambos")+SUMIFS('S5'!$I$6:$I$20,'S5'!$B$6:$B$20,$A6,'S5'!$E$6:$E$20,"Víctor")+SUMIFS('S5'!$I$6:$I$20,'S5'!$B$6:$B$20,$A6,'S5'!$E$6:$E$20,"Ambos")+SUMIFS('S6'!$I$6:$I$17,'S6'!$B$6:$B$17,$A6,'S6'!$E$6:$E$17,"Víctor")+SUMIFS('S6'!$I$6:$I$17,'S6'!$B$6:$B$17,$A6,'S6'!$E$6:$E$17,"Ambos")+SUMIFS('S7'!$I$6:$I$19,'S7'!$B$6:$B$19,$A6,'S7'!$E$6:$E$19,"Víctor")+SUMIFS('S7'!$I$6:$I$19,'S7'!$B$6:$B$19,$A6,'S7'!$E$6:$E$19,"Ambos")+SUMIFS('S8'!$I$6:$I$23,'S8'!$B$6:$B$23,$A6,'S8'!$E$6:$E$23,"Víctor")+SUMIFS('S8'!$I$6:$I$23,'S8'!$B$6:$B$23,$A6,'S8'!$E$6:$E$23,"Ambos")+SUMIFS('S9'!$I$6:$I$15,'S9'!$B$6:$B$15,$A6,'S9'!$E$6:$E$15,"Víctor")+SUMIFS('S9'!$I$6:$I$15,'S9'!$B$6:$B$15,$A6,'S9'!$E$6:$E$15,"Ambos")+SUMIFS('S10'!$I$6:$I$13,'S10'!$B$6:$B$13,$A6,'S10'!$E$6:$E$13,"Víctor")+SUMIFS('S10'!$I$6:$I$13,'S10'!$B$6:$B$13,$A6,'S10'!$E$6:$E$13,"Ambos")+SUMIFS('Holgura'!$I$6:$I$11,'Holgura'!$B$6:$B$11,$A6,'Holgura'!$E$6:$E$11,"Víctor")+SUMIFS('Holgura'!$I$6:$I$11,'Holgura'!$B$6:$B$11,$A6,'Holgura'!$E$6:$E$11,"Ambos")+SUMIFS('Entrega'!$I$6:$I$9,'Entrega'!$B$6:$B$9,$A6,'Entrega'!$E$6:$E$9,"Víctor")+SUMIFS('Entrega'!$I$6:$I$9,'Entrega'!$B$6:$B$9,$A6,'Entrega'!$E$6:$E$9,"Ambos")+SUMIFS('Defensa'!$I$6:$I$10,'Defensa'!$B$6:$B$10,$A6,'Defensa'!$E$6:$E$10,"Víctor")+SUMIFS('Defensa'!$I$6:$I$10,'Defensa'!$B$6:$B$10,$A6,'Defensa'!$E$6:$E$10,"Ambos")</f>
         <v/>
       </c>
       <c r="E6" s="21">
-        <f>SUMIFS('S1'!$I$6:$I$32,'S1'!$B$6:$B$32,$A6,'S1'!$E$6:$E$32,"Diego")+SUMIFS('S1'!$I$6:$I$32,'S1'!$B$6:$B$32,$A6,'S1'!$E$6:$E$32,"Ambos")+SUMIFS('S2'!$I$6:$I$23,'S2'!$B$6:$B$23,$A6,'S2'!$E$6:$E$23,"Diego")+SUMIFS('S2'!$I$6:$I$23,'S2'!$B$6:$B$23,$A6,'S2'!$E$6:$E$23,"Ambos")+SUMIFS('S3'!$I$6:$I$19,'S3'!$B$6:$B$19,$A6,'S3'!$E$6:$E$19,"Diego")+SUMIFS('S3'!$I$6:$I$19,'S3'!$B$6:$B$19,$A6,'S3'!$E$6:$E$19,"Ambos")+SUMIFS('S4'!$I$6:$I$20,'S4'!$B$6:$B$20,$A6,'S4'!$E$6:$E$20,"Diego")+SUMIFS('S4'!$I$6:$I$20,'S4'!$B$6:$B$20,$A6,'S4'!$E$6:$E$20,"Ambos")+SUMIFS('S5'!$I$6:$I$20,'S5'!$B$6:$B$20,$A6,'S5'!$E$6:$E$20,"Diego")+SUMIFS('S5'!$I$6:$I$20,'S5'!$B$6:$B$20,$A6,'S5'!$E$6:$E$20,"Ambos")+SUMIFS('S6'!$I$6:$I$17,'S6'!$B$6:$B$17,$A6,'S6'!$E$6:$E$17,"Diego")+SUMIFS('S6'!$I$6:$I$17,'S6'!$B$6:$B$17,$A6,'S6'!$E$6:$E$17,"Ambos")+SUMIFS('S7'!$I$6:$I$19,'S7'!$B$6:$B$19,$A6,'S7'!$E$6:$E$19,"Diego")+SUMIFS('S7'!$I$6:$I$19,'S7'!$B$6:$B$19,$A6,'S7'!$E$6:$E$19,"Ambos")+SUMIFS('S8'!$I$6:$I$23,'S8'!$B$6:$B$23,$A6,'S8'!$E$6:$E$23,"Diego")+SUMIFS('S8'!$I$6:$I$23,'S8'!$B$6:$B$23,$A6,'S8'!$E$6:$E$23,"Ambos")+SUMIFS('S9'!$I$6:$I$15,'S9'!$B$6:$B$15,$A6,'S9'!$E$6:$E$15,"Diego")+SUMIFS('S9'!$I$6:$I$15,'S9'!$B$6:$B$15,$A6,'S9'!$E$6:$E$15,"Ambos")+SUMIFS('S10'!$I$6:$I$13,'S10'!$B$6:$B$13,$A6,'S10'!$E$6:$E$13,"Diego")+SUMIFS('S10'!$I$6:$I$13,'S10'!$B$6:$B$13,$A6,'S10'!$E$6:$E$13,"Ambos")+SUMIFS('Holgura'!$I$6:$I$11,'Holgura'!$B$6:$B$11,$A6,'Holgura'!$E$6:$E$11,"Diego")+SUMIFS('Holgura'!$I$6:$I$11,'Holgura'!$B$6:$B$11,$A6,'Holgura'!$E$6:$E$11,"Ambos")+SUMIFS('Entrega'!$I$6:$I$9,'Entrega'!$B$6:$B$9,$A6,'Entrega'!$E$6:$E$9,"Diego")+SUMIFS('Entrega'!$I$6:$I$9,'Entrega'!$B$6:$B$9,$A6,'Entrega'!$E$6:$E$9,"Ambos")+SUMIFS('Defensa'!$I$6:$I$10,'Defensa'!$B$6:$B$10,$A6,'Defensa'!$E$6:$E$10,"Diego")+SUMIFS('Defensa'!$I$6:$I$10,'Defensa'!$B$6:$B$10,$A6,'Defensa'!$E$6:$E$10,"Ambos")</f>
+        <f>SUMIFS('S1'!$I$6:$I$32,'S1'!$B$6:$B$32,$A6,'S1'!$E$6:$E$32,"Diego")+SUMIFS('S1'!$I$6:$I$32,'S1'!$B$6:$B$32,$A6,'S1'!$E$6:$E$32,"Ambos")+SUMIFS('S2'!$I$6:$I$23,'S2'!$B$6:$B$23,$A6,'S2'!$E$6:$E$23,"Diego")+SUMIFS('S2'!$I$6:$I$23,'S2'!$B$6:$B$23,$A6,'S2'!$E$6:$E$23,"Ambos")+SUMIFS('S3'!$I$6:$I$24,'S3'!$B$6:$B$24,$A6,'S3'!$E$6:$E$24,"Diego")+SUMIFS('S3'!$I$6:$I$24,'S3'!$B$6:$B$24,$A6,'S3'!$E$6:$E$24,"Ambos")+SUMIFS('S4'!$I$6:$I$22,'S4'!$B$6:$B$22,$A6,'S4'!$E$6:$E$22,"Diego")+SUMIFS('S4'!$I$6:$I$22,'S4'!$B$6:$B$22,$A6,'S4'!$E$6:$E$22,"Ambos")+SUMIFS('S5'!$I$6:$I$20,'S5'!$B$6:$B$20,$A6,'S5'!$E$6:$E$20,"Diego")+SUMIFS('S5'!$I$6:$I$20,'S5'!$B$6:$B$20,$A6,'S5'!$E$6:$E$20,"Ambos")+SUMIFS('S6'!$I$6:$I$17,'S6'!$B$6:$B$17,$A6,'S6'!$E$6:$E$17,"Diego")+SUMIFS('S6'!$I$6:$I$17,'S6'!$B$6:$B$17,$A6,'S6'!$E$6:$E$17,"Ambos")+SUMIFS('S7'!$I$6:$I$19,'S7'!$B$6:$B$19,$A6,'S7'!$E$6:$E$19,"Diego")+SUMIFS('S7'!$I$6:$I$19,'S7'!$B$6:$B$19,$A6,'S7'!$E$6:$E$19,"Ambos")+SUMIFS('S8'!$I$6:$I$23,'S8'!$B$6:$B$23,$A6,'S8'!$E$6:$E$23,"Diego")+SUMIFS('S8'!$I$6:$I$23,'S8'!$B$6:$B$23,$A6,'S8'!$E$6:$E$23,"Ambos")+SUMIFS('S9'!$I$6:$I$15,'S9'!$B$6:$B$15,$A6,'S9'!$E$6:$E$15,"Diego")+SUMIFS('S9'!$I$6:$I$15,'S9'!$B$6:$B$15,$A6,'S9'!$E$6:$E$15,"Ambos")+SUMIFS('S10'!$I$6:$I$13,'S10'!$B$6:$B$13,$A6,'S10'!$E$6:$E$13,"Diego")+SUMIFS('S10'!$I$6:$I$13,'S10'!$B$6:$B$13,$A6,'S10'!$E$6:$E$13,"Ambos")+SUMIFS('Holgura'!$I$6:$I$11,'Holgura'!$B$6:$B$11,$A6,'Holgura'!$E$6:$E$11,"Diego")+SUMIFS('Holgura'!$I$6:$I$11,'Holgura'!$B$6:$B$11,$A6,'Holgura'!$E$6:$E$11,"Ambos")+SUMIFS('Entrega'!$I$6:$I$9,'Entrega'!$B$6:$B$9,$A6,'Entrega'!$E$6:$E$9,"Diego")+SUMIFS('Entrega'!$I$6:$I$9,'Entrega'!$B$6:$B$9,$A6,'Entrega'!$E$6:$E$9,"Ambos")+SUMIFS('Defensa'!$I$6:$I$10,'Defensa'!$B$6:$B$10,$A6,'Defensa'!$E$6:$E$10,"Diego")+SUMIFS('Defensa'!$I$6:$I$10,'Defensa'!$B$6:$B$10,$A6,'Defensa'!$E$6:$E$10,"Ambos")</f>
         <v/>
       </c>
       <c r="F6" s="21">
-        <f>COUNTIFS('S1'!$B$6:$B$32,$A6,'S1'!$E$6:$E$32,"Víctor")+COUNTIFS('S1'!$B$6:$B$32,$A6,'S1'!$E$6:$E$32,"Ambos")+COUNTIFS('S2'!$B$6:$B$23,$A6,'S2'!$E$6:$E$23,"Víctor")+COUNTIFS('S2'!$B$6:$B$23,$A6,'S2'!$E$6:$E$23,"Ambos")+COUNTIFS('S3'!$B$6:$B$19,$A6,'S3'!$E$6:$E$19,"Víctor")+COUNTIFS('S3'!$B$6:$B$19,$A6,'S3'!$E$6:$E$19,"Ambos")+COUNTIFS('S4'!$B$6:$B$20,$A6,'S4'!$E$6:$E$20,"Víctor")+COUNTIFS('S4'!$B$6:$B$20,$A6,'S4'!$E$6:$E$20,"Ambos")+COUNTIFS('S5'!$B$6:$B$20,$A6,'S5'!$E$6:$E$20,"Víctor")+COUNTIFS('S5'!$B$6:$B$20,$A6,'S5'!$E$6:$E$20,"Ambos")+COUNTIFS('S6'!$B$6:$B$17,$A6,'S6'!$E$6:$E$17,"Víctor")+COUNTIFS('S6'!$B$6:$B$17,$A6,'S6'!$E$6:$E$17,"Ambos")+COUNTIFS('S7'!$B$6:$B$19,$A6,'S7'!$E$6:$E$19,"Víctor")+COUNTIFS('S7'!$B$6:$B$19,$A6,'S7'!$E$6:$E$19,"Ambos")+COUNTIFS('S8'!$B$6:$B$23,$A6,'S8'!$E$6:$E$23,"Víctor")+COUNTIFS('S8'!$B$6:$B$23,$A6,'S8'!$E$6:$E$23,"Ambos")+COUNTIFS('S9'!$B$6:$B$15,$A6,'S9'!$E$6:$E$15,"Víctor")+COUNTIFS('S9'!$B$6:$B$15,$A6,'S9'!$E$6:$E$15,"Ambos")+COUNTIFS('S10'!$B$6:$B$13,$A6,'S10'!$E$6:$E$13,"Víctor")+COUNTIFS('S10'!$B$6:$B$13,$A6,'S10'!$E$6:$E$13,"Ambos")+COUNTIFS('Holgura'!$B$6:$B$11,$A6,'Holgura'!$E$6:$E$11,"Víctor")+COUNTIFS('Holgura'!$B$6:$B$11,$A6,'Holgura'!$E$6:$E$11,"Ambos")+COUNTIFS('Entrega'!$B$6:$B$9,$A6,'Entrega'!$E$6:$E$9,"Víctor")+COUNTIFS('Entrega'!$B$6:$B$9,$A6,'Entrega'!$E$6:$E$9,"Ambos")+COUNTIFS('Defensa'!$B$6:$B$10,$A6,'Defensa'!$E$6:$E$10,"Víctor")+COUNTIFS('Defensa'!$B$6:$B$10,$A6,'Defensa'!$E$6:$E$10,"Ambos")</f>
+        <f>COUNTIFS('S1'!$B$6:$B$32,$A6,'S1'!$E$6:$E$32,"Víctor")+COUNTIFS('S1'!$B$6:$B$32,$A6,'S1'!$E$6:$E$32,"Ambos")+COUNTIFS('S2'!$B$6:$B$23,$A6,'S2'!$E$6:$E$23,"Víctor")+COUNTIFS('S2'!$B$6:$B$23,$A6,'S2'!$E$6:$E$23,"Ambos")+COUNTIFS('S3'!$B$6:$B$24,$A6,'S3'!$E$6:$E$24,"Víctor")+COUNTIFS('S3'!$B$6:$B$24,$A6,'S3'!$E$6:$E$24,"Ambos")+COUNTIFS('S4'!$B$6:$B$22,$A6,'S4'!$E$6:$E$22,"Víctor")+COUNTIFS('S4'!$B$6:$B$22,$A6,'S4'!$E$6:$E$22,"Ambos")+COUNTIFS('S5'!$B$6:$B$20,$A6,'S5'!$E$6:$E$20,"Víctor")+COUNTIFS('S5'!$B$6:$B$20,$A6,'S5'!$E$6:$E$20,"Ambos")+COUNTIFS('S6'!$B$6:$B$17,$A6,'S6'!$E$6:$E$17,"Víctor")+COUNTIFS('S6'!$B$6:$B$17,$A6,'S6'!$E$6:$E$17,"Ambos")+COUNTIFS('S7'!$B$6:$B$19,$A6,'S7'!$E$6:$E$19,"Víctor")+COUNTIFS('S7'!$B$6:$B$19,$A6,'S7'!$E$6:$E$19,"Ambos")+COUNTIFS('S8'!$B$6:$B$23,$A6,'S8'!$E$6:$E$23,"Víctor")+COUNTIFS('S8'!$B$6:$B$23,$A6,'S8'!$E$6:$E$23,"Ambos")+COUNTIFS('S9'!$B$6:$B$15,$A6,'S9'!$E$6:$E$15,"Víctor")+COUNTIFS('S9'!$B$6:$B$15,$A6,'S9'!$E$6:$E$15,"Ambos")+COUNTIFS('S10'!$B$6:$B$13,$A6,'S10'!$E$6:$E$13,"Víctor")+COUNTIFS('S10'!$B$6:$B$13,$A6,'S10'!$E$6:$E$13,"Ambos")+COUNTIFS('Holgura'!$B$6:$B$11,$A6,'Holgura'!$E$6:$E$11,"Víctor")+COUNTIFS('Holgura'!$B$6:$B$11,$A6,'Holgura'!$E$6:$E$11,"Ambos")+COUNTIFS('Entrega'!$B$6:$B$9,$A6,'Entrega'!$E$6:$E$9,"Víctor")+COUNTIFS('Entrega'!$B$6:$B$9,$A6,'Entrega'!$E$6:$E$9,"Ambos")+COUNTIFS('Defensa'!$B$6:$B$10,$A6,'Defensa'!$E$6:$E$10,"Víctor")+COUNTIFS('Defensa'!$B$6:$B$10,$A6,'Defensa'!$E$6:$E$10,"Ambos")</f>
         <v/>
       </c>
       <c r="G6" s="21">
-        <f>COUNTIFS('S1'!$B$6:$B$32,$A6,'S1'!$E$6:$E$32,"Diego")+COUNTIFS('S1'!$B$6:$B$32,$A6,'S1'!$E$6:$E$32,"Ambos")+COUNTIFS('S2'!$B$6:$B$23,$A6,'S2'!$E$6:$E$23,"Diego")+COUNTIFS('S2'!$B$6:$B$23,$A6,'S2'!$E$6:$E$23,"Ambos")+COUNTIFS('S3'!$B$6:$B$19,$A6,'S3'!$E$6:$E$19,"Diego")+COUNTIFS('S3'!$B$6:$B$19,$A6,'S3'!$E$6:$E$19,"Ambos")+COUNTIFS('S4'!$B$6:$B$20,$A6,'S4'!$E$6:$E$20,"Diego")+COUNTIFS('S4'!$B$6:$B$20,$A6,'S4'!$E$6:$E$20,"Ambos")+COUNTIFS('S5'!$B$6:$B$20,$A6,'S5'!$E$6:$E$20,"Diego")+COUNTIFS('S5'!$B$6:$B$20,$A6,'S5'!$E$6:$E$20,"Ambos")+COUNTIFS('S6'!$B$6:$B$17,$A6,'S6'!$E$6:$E$17,"Diego")+COUNTIFS('S6'!$B$6:$B$17,$A6,'S6'!$E$6:$E$17,"Ambos")+COUNTIFS('S7'!$B$6:$B$19,$A6,'S7'!$E$6:$E$19,"Diego")+COUNTIFS('S7'!$B$6:$B$19,$A6,'S7'!$E$6:$E$19,"Ambos")+COUNTIFS('S8'!$B$6:$B$23,$A6,'S8'!$E$6:$E$23,"Diego")+COUNTIFS('S8'!$B$6:$B$23,$A6,'S8'!$E$6:$E$23,"Ambos")+COUNTIFS('S9'!$B$6:$B$15,$A6,'S9'!$E$6:$E$15,"Diego")+COUNTIFS('S9'!$B$6:$B$15,$A6,'S9'!$E$6:$E$15,"Ambos")+COUNTIFS('S10'!$B$6:$B$13,$A6,'S10'!$E$6:$E$13,"Diego")+COUNTIFS('S10'!$B$6:$B$13,$A6,'S10'!$E$6:$E$13,"Ambos")+COUNTIFS('Holgura'!$B$6:$B$11,$A6,'Holgura'!$E$6:$E$11,"Diego")+COUNTIFS('Holgura'!$B$6:$B$11,$A6,'Holgura'!$E$6:$E$11,"Ambos")+COUNTIFS('Entrega'!$B$6:$B$9,$A6,'Entrega'!$E$6:$E$9,"Diego")+COUNTIFS('Entrega'!$B$6:$B$9,$A6,'Entrega'!$E$6:$E$9,"Ambos")+COUNTIFS('Defensa'!$B$6:$B$10,$A6,'Defensa'!$E$6:$E$10,"Diego")+COUNTIFS('Defensa'!$B$6:$B$10,$A6,'Defensa'!$E$6:$E$10,"Ambos")</f>
+        <f>COUNTIFS('S1'!$B$6:$B$32,$A6,'S1'!$E$6:$E$32,"Diego")+COUNTIFS('S1'!$B$6:$B$32,$A6,'S1'!$E$6:$E$32,"Ambos")+COUNTIFS('S2'!$B$6:$B$23,$A6,'S2'!$E$6:$E$23,"Diego")+COUNTIFS('S2'!$B$6:$B$23,$A6,'S2'!$E$6:$E$23,"Ambos")+COUNTIFS('S3'!$B$6:$B$24,$A6,'S3'!$E$6:$E$24,"Diego")+COUNTIFS('S3'!$B$6:$B$24,$A6,'S3'!$E$6:$E$24,"Ambos")+COUNTIFS('S4'!$B$6:$B$22,$A6,'S4'!$E$6:$E$22,"Diego")+COUNTIFS('S4'!$B$6:$B$22,$A6,'S4'!$E$6:$E$22,"Ambos")+COUNTIFS('S5'!$B$6:$B$20,$A6,'S5'!$E$6:$E$20,"Diego")+COUNTIFS('S5'!$B$6:$B$20,$A6,'S5'!$E$6:$E$20,"Ambos")+COUNTIFS('S6'!$B$6:$B$17,$A6,'S6'!$E$6:$E$17,"Diego")+COUNTIFS('S6'!$B$6:$B$17,$A6,'S6'!$E$6:$E$17,"Ambos")+COUNTIFS('S7'!$B$6:$B$19,$A6,'S7'!$E$6:$E$19,"Diego")+COUNTIFS('S7'!$B$6:$B$19,$A6,'S7'!$E$6:$E$19,"Ambos")+COUNTIFS('S8'!$B$6:$B$23,$A6,'S8'!$E$6:$E$23,"Diego")+COUNTIFS('S8'!$B$6:$B$23,$A6,'S8'!$E$6:$E$23,"Ambos")+COUNTIFS('S9'!$B$6:$B$15,$A6,'S9'!$E$6:$E$15,"Diego")+COUNTIFS('S9'!$B$6:$B$15,$A6,'S9'!$E$6:$E$15,"Ambos")+COUNTIFS('S10'!$B$6:$B$13,$A6,'S10'!$E$6:$E$13,"Diego")+COUNTIFS('S10'!$B$6:$B$13,$A6,'S10'!$E$6:$E$13,"Ambos")+COUNTIFS('Holgura'!$B$6:$B$11,$A6,'Holgura'!$E$6:$E$11,"Diego")+COUNTIFS('Holgura'!$B$6:$B$11,$A6,'Holgura'!$E$6:$E$11,"Ambos")+COUNTIFS('Entrega'!$B$6:$B$9,$A6,'Entrega'!$E$6:$E$9,"Diego")+COUNTIFS('Entrega'!$B$6:$B$9,$A6,'Entrega'!$E$6:$E$9,"Ambos")+COUNTIFS('Defensa'!$B$6:$B$10,$A6,'Defensa'!$E$6:$E$10,"Diego")+COUNTIFS('Defensa'!$B$6:$B$10,$A6,'Defensa'!$E$6:$E$10,"Ambos")</f>
         <v/>
       </c>
     </row>
@@ -8738,19 +8759,19 @@
         <v/>
       </c>
       <c r="D7" s="21">
-        <f>SUMIFS('S1'!$I$6:$I$32,'S1'!$B$6:$B$32,$A7,'S1'!$E$6:$E$32,"Víctor")+SUMIFS('S1'!$I$6:$I$32,'S1'!$B$6:$B$32,$A7,'S1'!$E$6:$E$32,"Ambos")+SUMIFS('S2'!$I$6:$I$23,'S2'!$B$6:$B$23,$A7,'S2'!$E$6:$E$23,"Víctor")+SUMIFS('S2'!$I$6:$I$23,'S2'!$B$6:$B$23,$A7,'S2'!$E$6:$E$23,"Ambos")+SUMIFS('S3'!$I$6:$I$19,'S3'!$B$6:$B$19,$A7,'S3'!$E$6:$E$19,"Víctor")+SUMIFS('S3'!$I$6:$I$19,'S3'!$B$6:$B$19,$A7,'S3'!$E$6:$E$19,"Ambos")+SUMIFS('S4'!$I$6:$I$20,'S4'!$B$6:$B$20,$A7,'S4'!$E$6:$E$20,"Víctor")+SUMIFS('S4'!$I$6:$I$20,'S4'!$B$6:$B$20,$A7,'S4'!$E$6:$E$20,"Ambos")+SUMIFS('S5'!$I$6:$I$20,'S5'!$B$6:$B$20,$A7,'S5'!$E$6:$E$20,"Víctor")+SUMIFS('S5'!$I$6:$I$20,'S5'!$B$6:$B$20,$A7,'S5'!$E$6:$E$20,"Ambos")+SUMIFS('S6'!$I$6:$I$17,'S6'!$B$6:$B$17,$A7,'S6'!$E$6:$E$17,"Víctor")+SUMIFS('S6'!$I$6:$I$17,'S6'!$B$6:$B$17,$A7,'S6'!$E$6:$E$17,"Ambos")+SUMIFS('S7'!$I$6:$I$19,'S7'!$B$6:$B$19,$A7,'S7'!$E$6:$E$19,"Víctor")+SUMIFS('S7'!$I$6:$I$19,'S7'!$B$6:$B$19,$A7,'S7'!$E$6:$E$19,"Ambos")+SUMIFS('S8'!$I$6:$I$23,'S8'!$B$6:$B$23,$A7,'S8'!$E$6:$E$23,"Víctor")+SUMIFS('S8'!$I$6:$I$23,'S8'!$B$6:$B$23,$A7,'S8'!$E$6:$E$23,"Ambos")+SUMIFS('S9'!$I$6:$I$15,'S9'!$B$6:$B$15,$A7,'S9'!$E$6:$E$15,"Víctor")+SUMIFS('S9'!$I$6:$I$15,'S9'!$B$6:$B$15,$A7,'S9'!$E$6:$E$15,"Ambos")+SUMIFS('S10'!$I$6:$I$13,'S10'!$B$6:$B$13,$A7,'S10'!$E$6:$E$13,"Víctor")+SUMIFS('S10'!$I$6:$I$13,'S10'!$B$6:$B$13,$A7,'S10'!$E$6:$E$13,"Ambos")+SUMIFS('Holgura'!$I$6:$I$11,'Holgura'!$B$6:$B$11,$A7,'Holgura'!$E$6:$E$11,"Víctor")+SUMIFS('Holgura'!$I$6:$I$11,'Holgura'!$B$6:$B$11,$A7,'Holgura'!$E$6:$E$11,"Ambos")+SUMIFS('Entrega'!$I$6:$I$9,'Entrega'!$B$6:$B$9,$A7,'Entrega'!$E$6:$E$9,"Víctor")+SUMIFS('Entrega'!$I$6:$I$9,'Entrega'!$B$6:$B$9,$A7,'Entrega'!$E$6:$E$9,"Ambos")+SUMIFS('Defensa'!$I$6:$I$10,'Defensa'!$B$6:$B$10,$A7,'Defensa'!$E$6:$E$10,"Víctor")+SUMIFS('Defensa'!$I$6:$I$10,'Defensa'!$B$6:$B$10,$A7,'Defensa'!$E$6:$E$10,"Ambos")</f>
+        <f>SUMIFS('S1'!$I$6:$I$32,'S1'!$B$6:$B$32,$A7,'S1'!$E$6:$E$32,"Víctor")+SUMIFS('S1'!$I$6:$I$32,'S1'!$B$6:$B$32,$A7,'S1'!$E$6:$E$32,"Ambos")+SUMIFS('S2'!$I$6:$I$23,'S2'!$B$6:$B$23,$A7,'S2'!$E$6:$E$23,"Víctor")+SUMIFS('S2'!$I$6:$I$23,'S2'!$B$6:$B$23,$A7,'S2'!$E$6:$E$23,"Ambos")+SUMIFS('S3'!$I$6:$I$24,'S3'!$B$6:$B$24,$A7,'S3'!$E$6:$E$24,"Víctor")+SUMIFS('S3'!$I$6:$I$24,'S3'!$B$6:$B$24,$A7,'S3'!$E$6:$E$24,"Ambos")+SUMIFS('S4'!$I$6:$I$22,'S4'!$B$6:$B$22,$A7,'S4'!$E$6:$E$22,"Víctor")+SUMIFS('S4'!$I$6:$I$22,'S4'!$B$6:$B$22,$A7,'S4'!$E$6:$E$22,"Ambos")+SUMIFS('S5'!$I$6:$I$20,'S5'!$B$6:$B$20,$A7,'S5'!$E$6:$E$20,"Víctor")+SUMIFS('S5'!$I$6:$I$20,'S5'!$B$6:$B$20,$A7,'S5'!$E$6:$E$20,"Ambos")+SUMIFS('S6'!$I$6:$I$17,'S6'!$B$6:$B$17,$A7,'S6'!$E$6:$E$17,"Víctor")+SUMIFS('S6'!$I$6:$I$17,'S6'!$B$6:$B$17,$A7,'S6'!$E$6:$E$17,"Ambos")+SUMIFS('S7'!$I$6:$I$19,'S7'!$B$6:$B$19,$A7,'S7'!$E$6:$E$19,"Víctor")+SUMIFS('S7'!$I$6:$I$19,'S7'!$B$6:$B$19,$A7,'S7'!$E$6:$E$19,"Ambos")+SUMIFS('S8'!$I$6:$I$23,'S8'!$B$6:$B$23,$A7,'S8'!$E$6:$E$23,"Víctor")+SUMIFS('S8'!$I$6:$I$23,'S8'!$B$6:$B$23,$A7,'S8'!$E$6:$E$23,"Ambos")+SUMIFS('S9'!$I$6:$I$15,'S9'!$B$6:$B$15,$A7,'S9'!$E$6:$E$15,"Víctor")+SUMIFS('S9'!$I$6:$I$15,'S9'!$B$6:$B$15,$A7,'S9'!$E$6:$E$15,"Ambos")+SUMIFS('S10'!$I$6:$I$13,'S10'!$B$6:$B$13,$A7,'S10'!$E$6:$E$13,"Víctor")+SUMIFS('S10'!$I$6:$I$13,'S10'!$B$6:$B$13,$A7,'S10'!$E$6:$E$13,"Ambos")+SUMIFS('Holgura'!$I$6:$I$11,'Holgura'!$B$6:$B$11,$A7,'Holgura'!$E$6:$E$11,"Víctor")+SUMIFS('Holgura'!$I$6:$I$11,'Holgura'!$B$6:$B$11,$A7,'Holgura'!$E$6:$E$11,"Ambos")+SUMIFS('Entrega'!$I$6:$I$9,'Entrega'!$B$6:$B$9,$A7,'Entrega'!$E$6:$E$9,"Víctor")+SUMIFS('Entrega'!$I$6:$I$9,'Entrega'!$B$6:$B$9,$A7,'Entrega'!$E$6:$E$9,"Ambos")+SUMIFS('Defensa'!$I$6:$I$10,'Defensa'!$B$6:$B$10,$A7,'Defensa'!$E$6:$E$10,"Víctor")+SUMIFS('Defensa'!$I$6:$I$10,'Defensa'!$B$6:$B$10,$A7,'Defensa'!$E$6:$E$10,"Ambos")</f>
         <v/>
       </c>
       <c r="E7" s="21">
-        <f>SUMIFS('S1'!$I$6:$I$32,'S1'!$B$6:$B$32,$A7,'S1'!$E$6:$E$32,"Diego")+SUMIFS('S1'!$I$6:$I$32,'S1'!$B$6:$B$32,$A7,'S1'!$E$6:$E$32,"Ambos")+SUMIFS('S2'!$I$6:$I$23,'S2'!$B$6:$B$23,$A7,'S2'!$E$6:$E$23,"Diego")+SUMIFS('S2'!$I$6:$I$23,'S2'!$B$6:$B$23,$A7,'S2'!$E$6:$E$23,"Ambos")+SUMIFS('S3'!$I$6:$I$19,'S3'!$B$6:$B$19,$A7,'S3'!$E$6:$E$19,"Diego")+SUMIFS('S3'!$I$6:$I$19,'S3'!$B$6:$B$19,$A7,'S3'!$E$6:$E$19,"Ambos")+SUMIFS('S4'!$I$6:$I$20,'S4'!$B$6:$B$20,$A7,'S4'!$E$6:$E$20,"Diego")+SUMIFS('S4'!$I$6:$I$20,'S4'!$B$6:$B$20,$A7,'S4'!$E$6:$E$20,"Ambos")+SUMIFS('S5'!$I$6:$I$20,'S5'!$B$6:$B$20,$A7,'S5'!$E$6:$E$20,"Diego")+SUMIFS('S5'!$I$6:$I$20,'S5'!$B$6:$B$20,$A7,'S5'!$E$6:$E$20,"Ambos")+SUMIFS('S6'!$I$6:$I$17,'S6'!$B$6:$B$17,$A7,'S6'!$E$6:$E$17,"Diego")+SUMIFS('S6'!$I$6:$I$17,'S6'!$B$6:$B$17,$A7,'S6'!$E$6:$E$17,"Ambos")+SUMIFS('S7'!$I$6:$I$19,'S7'!$B$6:$B$19,$A7,'S7'!$E$6:$E$19,"Diego")+SUMIFS('S7'!$I$6:$I$19,'S7'!$B$6:$B$19,$A7,'S7'!$E$6:$E$19,"Ambos")+SUMIFS('S8'!$I$6:$I$23,'S8'!$B$6:$B$23,$A7,'S8'!$E$6:$E$23,"Diego")+SUMIFS('S8'!$I$6:$I$23,'S8'!$B$6:$B$23,$A7,'S8'!$E$6:$E$23,"Ambos")+SUMIFS('S9'!$I$6:$I$15,'S9'!$B$6:$B$15,$A7,'S9'!$E$6:$E$15,"Diego")+SUMIFS('S9'!$I$6:$I$15,'S9'!$B$6:$B$15,$A7,'S9'!$E$6:$E$15,"Ambos")+SUMIFS('S10'!$I$6:$I$13,'S10'!$B$6:$B$13,$A7,'S10'!$E$6:$E$13,"Diego")+SUMIFS('S10'!$I$6:$I$13,'S10'!$B$6:$B$13,$A7,'S10'!$E$6:$E$13,"Ambos")+SUMIFS('Holgura'!$I$6:$I$11,'Holgura'!$B$6:$B$11,$A7,'Holgura'!$E$6:$E$11,"Diego")+SUMIFS('Holgura'!$I$6:$I$11,'Holgura'!$B$6:$B$11,$A7,'Holgura'!$E$6:$E$11,"Ambos")+SUMIFS('Entrega'!$I$6:$I$9,'Entrega'!$B$6:$B$9,$A7,'Entrega'!$E$6:$E$9,"Diego")+SUMIFS('Entrega'!$I$6:$I$9,'Entrega'!$B$6:$B$9,$A7,'Entrega'!$E$6:$E$9,"Ambos")+SUMIFS('Defensa'!$I$6:$I$10,'Defensa'!$B$6:$B$10,$A7,'Defensa'!$E$6:$E$10,"Diego")+SUMIFS('Defensa'!$I$6:$I$10,'Defensa'!$B$6:$B$10,$A7,'Defensa'!$E$6:$E$10,"Ambos")</f>
+        <f>SUMIFS('S1'!$I$6:$I$32,'S1'!$B$6:$B$32,$A7,'S1'!$E$6:$E$32,"Diego")+SUMIFS('S1'!$I$6:$I$32,'S1'!$B$6:$B$32,$A7,'S1'!$E$6:$E$32,"Ambos")+SUMIFS('S2'!$I$6:$I$23,'S2'!$B$6:$B$23,$A7,'S2'!$E$6:$E$23,"Diego")+SUMIFS('S2'!$I$6:$I$23,'S2'!$B$6:$B$23,$A7,'S2'!$E$6:$E$23,"Ambos")+SUMIFS('S3'!$I$6:$I$24,'S3'!$B$6:$B$24,$A7,'S3'!$E$6:$E$24,"Diego")+SUMIFS('S3'!$I$6:$I$24,'S3'!$B$6:$B$24,$A7,'S3'!$E$6:$E$24,"Ambos")+SUMIFS('S4'!$I$6:$I$22,'S4'!$B$6:$B$22,$A7,'S4'!$E$6:$E$22,"Diego")+SUMIFS('S4'!$I$6:$I$22,'S4'!$B$6:$B$22,$A7,'S4'!$E$6:$E$22,"Ambos")+SUMIFS('S5'!$I$6:$I$20,'S5'!$B$6:$B$20,$A7,'S5'!$E$6:$E$20,"Diego")+SUMIFS('S5'!$I$6:$I$20,'S5'!$B$6:$B$20,$A7,'S5'!$E$6:$E$20,"Ambos")+SUMIFS('S6'!$I$6:$I$17,'S6'!$B$6:$B$17,$A7,'S6'!$E$6:$E$17,"Diego")+SUMIFS('S6'!$I$6:$I$17,'S6'!$B$6:$B$17,$A7,'S6'!$E$6:$E$17,"Ambos")+SUMIFS('S7'!$I$6:$I$19,'S7'!$B$6:$B$19,$A7,'S7'!$E$6:$E$19,"Diego")+SUMIFS('S7'!$I$6:$I$19,'S7'!$B$6:$B$19,$A7,'S7'!$E$6:$E$19,"Ambos")+SUMIFS('S8'!$I$6:$I$23,'S8'!$B$6:$B$23,$A7,'S8'!$E$6:$E$23,"Diego")+SUMIFS('S8'!$I$6:$I$23,'S8'!$B$6:$B$23,$A7,'S8'!$E$6:$E$23,"Ambos")+SUMIFS('S9'!$I$6:$I$15,'S9'!$B$6:$B$15,$A7,'S9'!$E$6:$E$15,"Diego")+SUMIFS('S9'!$I$6:$I$15,'S9'!$B$6:$B$15,$A7,'S9'!$E$6:$E$15,"Ambos")+SUMIFS('S10'!$I$6:$I$13,'S10'!$B$6:$B$13,$A7,'S10'!$E$6:$E$13,"Diego")+SUMIFS('S10'!$I$6:$I$13,'S10'!$B$6:$B$13,$A7,'S10'!$E$6:$E$13,"Ambos")+SUMIFS('Holgura'!$I$6:$I$11,'Holgura'!$B$6:$B$11,$A7,'Holgura'!$E$6:$E$11,"Diego")+SUMIFS('Holgura'!$I$6:$I$11,'Holgura'!$B$6:$B$11,$A7,'Holgura'!$E$6:$E$11,"Ambos")+SUMIFS('Entrega'!$I$6:$I$9,'Entrega'!$B$6:$B$9,$A7,'Entrega'!$E$6:$E$9,"Diego")+SUMIFS('Entrega'!$I$6:$I$9,'Entrega'!$B$6:$B$9,$A7,'Entrega'!$E$6:$E$9,"Ambos")+SUMIFS('Defensa'!$I$6:$I$10,'Defensa'!$B$6:$B$10,$A7,'Defensa'!$E$6:$E$10,"Diego")+SUMIFS('Defensa'!$I$6:$I$10,'Defensa'!$B$6:$B$10,$A7,'Defensa'!$E$6:$E$10,"Ambos")</f>
         <v/>
       </c>
       <c r="F7" s="21">
-        <f>COUNTIFS('S1'!$B$6:$B$32,$A7,'S1'!$E$6:$E$32,"Víctor")+COUNTIFS('S1'!$B$6:$B$32,$A7,'S1'!$E$6:$E$32,"Ambos")+COUNTIFS('S2'!$B$6:$B$23,$A7,'S2'!$E$6:$E$23,"Víctor")+COUNTIFS('S2'!$B$6:$B$23,$A7,'S2'!$E$6:$E$23,"Ambos")+COUNTIFS('S3'!$B$6:$B$19,$A7,'S3'!$E$6:$E$19,"Víctor")+COUNTIFS('S3'!$B$6:$B$19,$A7,'S3'!$E$6:$E$19,"Ambos")+COUNTIFS('S4'!$B$6:$B$20,$A7,'S4'!$E$6:$E$20,"Víctor")+COUNTIFS('S4'!$B$6:$B$20,$A7,'S4'!$E$6:$E$20,"Ambos")+COUNTIFS('S5'!$B$6:$B$20,$A7,'S5'!$E$6:$E$20,"Víctor")+COUNTIFS('S5'!$B$6:$B$20,$A7,'S5'!$E$6:$E$20,"Ambos")+COUNTIFS('S6'!$B$6:$B$17,$A7,'S6'!$E$6:$E$17,"Víctor")+COUNTIFS('S6'!$B$6:$B$17,$A7,'S6'!$E$6:$E$17,"Ambos")+COUNTIFS('S7'!$B$6:$B$19,$A7,'S7'!$E$6:$E$19,"Víctor")+COUNTIFS('S7'!$B$6:$B$19,$A7,'S7'!$E$6:$E$19,"Ambos")+COUNTIFS('S8'!$B$6:$B$23,$A7,'S8'!$E$6:$E$23,"Víctor")+COUNTIFS('S8'!$B$6:$B$23,$A7,'S8'!$E$6:$E$23,"Ambos")+COUNTIFS('S9'!$B$6:$B$15,$A7,'S9'!$E$6:$E$15,"Víctor")+COUNTIFS('S9'!$B$6:$B$15,$A7,'S9'!$E$6:$E$15,"Ambos")+COUNTIFS('S10'!$B$6:$B$13,$A7,'S10'!$E$6:$E$13,"Víctor")+COUNTIFS('S10'!$B$6:$B$13,$A7,'S10'!$E$6:$E$13,"Ambos")+COUNTIFS('Holgura'!$B$6:$B$11,$A7,'Holgura'!$E$6:$E$11,"Víctor")+COUNTIFS('Holgura'!$B$6:$B$11,$A7,'Holgura'!$E$6:$E$11,"Ambos")+COUNTIFS('Entrega'!$B$6:$B$9,$A7,'Entrega'!$E$6:$E$9,"Víctor")+COUNTIFS('Entrega'!$B$6:$B$9,$A7,'Entrega'!$E$6:$E$9,"Ambos")+COUNTIFS('Defensa'!$B$6:$B$10,$A7,'Defensa'!$E$6:$E$10,"Víctor")+COUNTIFS('Defensa'!$B$6:$B$10,$A7,'Defensa'!$E$6:$E$10,"Ambos")</f>
+        <f>COUNTIFS('S1'!$B$6:$B$32,$A7,'S1'!$E$6:$E$32,"Víctor")+COUNTIFS('S1'!$B$6:$B$32,$A7,'S1'!$E$6:$E$32,"Ambos")+COUNTIFS('S2'!$B$6:$B$23,$A7,'S2'!$E$6:$E$23,"Víctor")+COUNTIFS('S2'!$B$6:$B$23,$A7,'S2'!$E$6:$E$23,"Ambos")+COUNTIFS('S3'!$B$6:$B$24,$A7,'S3'!$E$6:$E$24,"Víctor")+COUNTIFS('S3'!$B$6:$B$24,$A7,'S3'!$E$6:$E$24,"Ambos")+COUNTIFS('S4'!$B$6:$B$22,$A7,'S4'!$E$6:$E$22,"Víctor")+COUNTIFS('S4'!$B$6:$B$22,$A7,'S4'!$E$6:$E$22,"Ambos")+COUNTIFS('S5'!$B$6:$B$20,$A7,'S5'!$E$6:$E$20,"Víctor")+COUNTIFS('S5'!$B$6:$B$20,$A7,'S5'!$E$6:$E$20,"Ambos")+COUNTIFS('S6'!$B$6:$B$17,$A7,'S6'!$E$6:$E$17,"Víctor")+COUNTIFS('S6'!$B$6:$B$17,$A7,'S6'!$E$6:$E$17,"Ambos")+COUNTIFS('S7'!$B$6:$B$19,$A7,'S7'!$E$6:$E$19,"Víctor")+COUNTIFS('S7'!$B$6:$B$19,$A7,'S7'!$E$6:$E$19,"Ambos")+COUNTIFS('S8'!$B$6:$B$23,$A7,'S8'!$E$6:$E$23,"Víctor")+COUNTIFS('S8'!$B$6:$B$23,$A7,'S8'!$E$6:$E$23,"Ambos")+COUNTIFS('S9'!$B$6:$B$15,$A7,'S9'!$E$6:$E$15,"Víctor")+COUNTIFS('S9'!$B$6:$B$15,$A7,'S9'!$E$6:$E$15,"Ambos")+COUNTIFS('S10'!$B$6:$B$13,$A7,'S10'!$E$6:$E$13,"Víctor")+COUNTIFS('S10'!$B$6:$B$13,$A7,'S10'!$E$6:$E$13,"Ambos")+COUNTIFS('Holgura'!$B$6:$B$11,$A7,'Holgura'!$E$6:$E$11,"Víctor")+COUNTIFS('Holgura'!$B$6:$B$11,$A7,'Holgura'!$E$6:$E$11,"Ambos")+COUNTIFS('Entrega'!$B$6:$B$9,$A7,'Entrega'!$E$6:$E$9,"Víctor")+COUNTIFS('Entrega'!$B$6:$B$9,$A7,'Entrega'!$E$6:$E$9,"Ambos")+COUNTIFS('Defensa'!$B$6:$B$10,$A7,'Defensa'!$E$6:$E$10,"Víctor")+COUNTIFS('Defensa'!$B$6:$B$10,$A7,'Defensa'!$E$6:$E$10,"Ambos")</f>
         <v/>
       </c>
       <c r="G7" s="21">
-        <f>COUNTIFS('S1'!$B$6:$B$32,$A7,'S1'!$E$6:$E$32,"Diego")+COUNTIFS('S1'!$B$6:$B$32,$A7,'S1'!$E$6:$E$32,"Ambos")+COUNTIFS('S2'!$B$6:$B$23,$A7,'S2'!$E$6:$E$23,"Diego")+COUNTIFS('S2'!$B$6:$B$23,$A7,'S2'!$E$6:$E$23,"Ambos")+COUNTIFS('S3'!$B$6:$B$19,$A7,'S3'!$E$6:$E$19,"Diego")+COUNTIFS('S3'!$B$6:$B$19,$A7,'S3'!$E$6:$E$19,"Ambos")+COUNTIFS('S4'!$B$6:$B$20,$A7,'S4'!$E$6:$E$20,"Diego")+COUNTIFS('S4'!$B$6:$B$20,$A7,'S4'!$E$6:$E$20,"Ambos")+COUNTIFS('S5'!$B$6:$B$20,$A7,'S5'!$E$6:$E$20,"Diego")+COUNTIFS('S5'!$B$6:$B$20,$A7,'S5'!$E$6:$E$20,"Ambos")+COUNTIFS('S6'!$B$6:$B$17,$A7,'S6'!$E$6:$E$17,"Diego")+COUNTIFS('S6'!$B$6:$B$17,$A7,'S6'!$E$6:$E$17,"Ambos")+COUNTIFS('S7'!$B$6:$B$19,$A7,'S7'!$E$6:$E$19,"Diego")+COUNTIFS('S7'!$B$6:$B$19,$A7,'S7'!$E$6:$E$19,"Ambos")+COUNTIFS('S8'!$B$6:$B$23,$A7,'S8'!$E$6:$E$23,"Diego")+COUNTIFS('S8'!$B$6:$B$23,$A7,'S8'!$E$6:$E$23,"Ambos")+COUNTIFS('S9'!$B$6:$B$15,$A7,'S9'!$E$6:$E$15,"Diego")+COUNTIFS('S9'!$B$6:$B$15,$A7,'S9'!$E$6:$E$15,"Ambos")+COUNTIFS('S10'!$B$6:$B$13,$A7,'S10'!$E$6:$E$13,"Diego")+COUNTIFS('S10'!$B$6:$B$13,$A7,'S10'!$E$6:$E$13,"Ambos")+COUNTIFS('Holgura'!$B$6:$B$11,$A7,'Holgura'!$E$6:$E$11,"Diego")+COUNTIFS('Holgura'!$B$6:$B$11,$A7,'Holgura'!$E$6:$E$11,"Ambos")+COUNTIFS('Entrega'!$B$6:$B$9,$A7,'Entrega'!$E$6:$E$9,"Diego")+COUNTIFS('Entrega'!$B$6:$B$9,$A7,'Entrega'!$E$6:$E$9,"Ambos")+COUNTIFS('Defensa'!$B$6:$B$10,$A7,'Defensa'!$E$6:$E$10,"Diego")+COUNTIFS('Defensa'!$B$6:$B$10,$A7,'Defensa'!$E$6:$E$10,"Ambos")</f>
+        <f>COUNTIFS('S1'!$B$6:$B$32,$A7,'S1'!$E$6:$E$32,"Diego")+COUNTIFS('S1'!$B$6:$B$32,$A7,'S1'!$E$6:$E$32,"Ambos")+COUNTIFS('S2'!$B$6:$B$23,$A7,'S2'!$E$6:$E$23,"Diego")+COUNTIFS('S2'!$B$6:$B$23,$A7,'S2'!$E$6:$E$23,"Ambos")+COUNTIFS('S3'!$B$6:$B$24,$A7,'S3'!$E$6:$E$24,"Diego")+COUNTIFS('S3'!$B$6:$B$24,$A7,'S3'!$E$6:$E$24,"Ambos")+COUNTIFS('S4'!$B$6:$B$22,$A7,'S4'!$E$6:$E$22,"Diego")+COUNTIFS('S4'!$B$6:$B$22,$A7,'S4'!$E$6:$E$22,"Ambos")+COUNTIFS('S5'!$B$6:$B$20,$A7,'S5'!$E$6:$E$20,"Diego")+COUNTIFS('S5'!$B$6:$B$20,$A7,'S5'!$E$6:$E$20,"Ambos")+COUNTIFS('S6'!$B$6:$B$17,$A7,'S6'!$E$6:$E$17,"Diego")+COUNTIFS('S6'!$B$6:$B$17,$A7,'S6'!$E$6:$E$17,"Ambos")+COUNTIFS('S7'!$B$6:$B$19,$A7,'S7'!$E$6:$E$19,"Diego")+COUNTIFS('S7'!$B$6:$B$19,$A7,'S7'!$E$6:$E$19,"Ambos")+COUNTIFS('S8'!$B$6:$B$23,$A7,'S8'!$E$6:$E$23,"Diego")+COUNTIFS('S8'!$B$6:$B$23,$A7,'S8'!$E$6:$E$23,"Ambos")+COUNTIFS('S9'!$B$6:$B$15,$A7,'S9'!$E$6:$E$15,"Diego")+COUNTIFS('S9'!$B$6:$B$15,$A7,'S9'!$E$6:$E$15,"Ambos")+COUNTIFS('S10'!$B$6:$B$13,$A7,'S10'!$E$6:$E$13,"Diego")+COUNTIFS('S10'!$B$6:$B$13,$A7,'S10'!$E$6:$E$13,"Ambos")+COUNTIFS('Holgura'!$B$6:$B$11,$A7,'Holgura'!$E$6:$E$11,"Diego")+COUNTIFS('Holgura'!$B$6:$B$11,$A7,'Holgura'!$E$6:$E$11,"Ambos")+COUNTIFS('Entrega'!$B$6:$B$9,$A7,'Entrega'!$E$6:$E$9,"Diego")+COUNTIFS('Entrega'!$B$6:$B$9,$A7,'Entrega'!$E$6:$E$9,"Ambos")+COUNTIFS('Defensa'!$B$6:$B$10,$A7,'Defensa'!$E$6:$E$10,"Diego")+COUNTIFS('Defensa'!$B$6:$B$10,$A7,'Defensa'!$E$6:$E$10,"Ambos")</f>
         <v/>
       </c>
     </row>
@@ -8767,19 +8788,19 @@
         <v/>
       </c>
       <c r="D8" s="21">
-        <f>SUMIFS('S1'!$I$6:$I$32,'S1'!$B$6:$B$32,$A8,'S1'!$E$6:$E$32,"Víctor")+SUMIFS('S1'!$I$6:$I$32,'S1'!$B$6:$B$32,$A8,'S1'!$E$6:$E$32,"Ambos")+SUMIFS('S2'!$I$6:$I$23,'S2'!$B$6:$B$23,$A8,'S2'!$E$6:$E$23,"Víctor")+SUMIFS('S2'!$I$6:$I$23,'S2'!$B$6:$B$23,$A8,'S2'!$E$6:$E$23,"Ambos")+SUMIFS('S3'!$I$6:$I$19,'S3'!$B$6:$B$19,$A8,'S3'!$E$6:$E$19,"Víctor")+SUMIFS('S3'!$I$6:$I$19,'S3'!$B$6:$B$19,$A8,'S3'!$E$6:$E$19,"Ambos")+SUMIFS('S4'!$I$6:$I$20,'S4'!$B$6:$B$20,$A8,'S4'!$E$6:$E$20,"Víctor")+SUMIFS('S4'!$I$6:$I$20,'S4'!$B$6:$B$20,$A8,'S4'!$E$6:$E$20,"Ambos")+SUMIFS('S5'!$I$6:$I$20,'S5'!$B$6:$B$20,$A8,'S5'!$E$6:$E$20,"Víctor")+SUMIFS('S5'!$I$6:$I$20,'S5'!$B$6:$B$20,$A8,'S5'!$E$6:$E$20,"Ambos")+SUMIFS('S6'!$I$6:$I$17,'S6'!$B$6:$B$17,$A8,'S6'!$E$6:$E$17,"Víctor")+SUMIFS('S6'!$I$6:$I$17,'S6'!$B$6:$B$17,$A8,'S6'!$E$6:$E$17,"Ambos")+SUMIFS('S7'!$I$6:$I$19,'S7'!$B$6:$B$19,$A8,'S7'!$E$6:$E$19,"Víctor")+SUMIFS('S7'!$I$6:$I$19,'S7'!$B$6:$B$19,$A8,'S7'!$E$6:$E$19,"Ambos")+SUMIFS('S8'!$I$6:$I$23,'S8'!$B$6:$B$23,$A8,'S8'!$E$6:$E$23,"Víctor")+SUMIFS('S8'!$I$6:$I$23,'S8'!$B$6:$B$23,$A8,'S8'!$E$6:$E$23,"Ambos")+SUMIFS('S9'!$I$6:$I$15,'S9'!$B$6:$B$15,$A8,'S9'!$E$6:$E$15,"Víctor")+SUMIFS('S9'!$I$6:$I$15,'S9'!$B$6:$B$15,$A8,'S9'!$E$6:$E$15,"Ambos")+SUMIFS('S10'!$I$6:$I$13,'S10'!$B$6:$B$13,$A8,'S10'!$E$6:$E$13,"Víctor")+SUMIFS('S10'!$I$6:$I$13,'S10'!$B$6:$B$13,$A8,'S10'!$E$6:$E$13,"Ambos")+SUMIFS('Holgura'!$I$6:$I$11,'Holgura'!$B$6:$B$11,$A8,'Holgura'!$E$6:$E$11,"Víctor")+SUMIFS('Holgura'!$I$6:$I$11,'Holgura'!$B$6:$B$11,$A8,'Holgura'!$E$6:$E$11,"Ambos")+SUMIFS('Entrega'!$I$6:$I$9,'Entrega'!$B$6:$B$9,$A8,'Entrega'!$E$6:$E$9,"Víctor")+SUMIFS('Entrega'!$I$6:$I$9,'Entrega'!$B$6:$B$9,$A8,'Entrega'!$E$6:$E$9,"Ambos")+SUMIFS('Defensa'!$I$6:$I$10,'Defensa'!$B$6:$B$10,$A8,'Defensa'!$E$6:$E$10,"Víctor")+SUMIFS('Defensa'!$I$6:$I$10,'Defensa'!$B$6:$B$10,$A8,'Defensa'!$E$6:$E$10,"Ambos")</f>
+        <f>SUMIFS('S1'!$I$6:$I$32,'S1'!$B$6:$B$32,$A8,'S1'!$E$6:$E$32,"Víctor")+SUMIFS('S1'!$I$6:$I$32,'S1'!$B$6:$B$32,$A8,'S1'!$E$6:$E$32,"Ambos")+SUMIFS('S2'!$I$6:$I$23,'S2'!$B$6:$B$23,$A8,'S2'!$E$6:$E$23,"Víctor")+SUMIFS('S2'!$I$6:$I$23,'S2'!$B$6:$B$23,$A8,'S2'!$E$6:$E$23,"Ambos")+SUMIFS('S3'!$I$6:$I$24,'S3'!$B$6:$B$24,$A8,'S3'!$E$6:$E$24,"Víctor")+SUMIFS('S3'!$I$6:$I$24,'S3'!$B$6:$B$24,$A8,'S3'!$E$6:$E$24,"Ambos")+SUMIFS('S4'!$I$6:$I$22,'S4'!$B$6:$B$22,$A8,'S4'!$E$6:$E$22,"Víctor")+SUMIFS('S4'!$I$6:$I$22,'S4'!$B$6:$B$22,$A8,'S4'!$E$6:$E$22,"Ambos")+SUMIFS('S5'!$I$6:$I$20,'S5'!$B$6:$B$20,$A8,'S5'!$E$6:$E$20,"Víctor")+SUMIFS('S5'!$I$6:$I$20,'S5'!$B$6:$B$20,$A8,'S5'!$E$6:$E$20,"Ambos")+SUMIFS('S6'!$I$6:$I$17,'S6'!$B$6:$B$17,$A8,'S6'!$E$6:$E$17,"Víctor")+SUMIFS('S6'!$I$6:$I$17,'S6'!$B$6:$B$17,$A8,'S6'!$E$6:$E$17,"Ambos")+SUMIFS('S7'!$I$6:$I$19,'S7'!$B$6:$B$19,$A8,'S7'!$E$6:$E$19,"Víctor")+SUMIFS('S7'!$I$6:$I$19,'S7'!$B$6:$B$19,$A8,'S7'!$E$6:$E$19,"Ambos")+SUMIFS('S8'!$I$6:$I$23,'S8'!$B$6:$B$23,$A8,'S8'!$E$6:$E$23,"Víctor")+SUMIFS('S8'!$I$6:$I$23,'S8'!$B$6:$B$23,$A8,'S8'!$E$6:$E$23,"Ambos")+SUMIFS('S9'!$I$6:$I$15,'S9'!$B$6:$B$15,$A8,'S9'!$E$6:$E$15,"Víctor")+SUMIFS('S9'!$I$6:$I$15,'S9'!$B$6:$B$15,$A8,'S9'!$E$6:$E$15,"Ambos")+SUMIFS('S10'!$I$6:$I$13,'S10'!$B$6:$B$13,$A8,'S10'!$E$6:$E$13,"Víctor")+SUMIFS('S10'!$I$6:$I$13,'S10'!$B$6:$B$13,$A8,'S10'!$E$6:$E$13,"Ambos")+SUMIFS('Holgura'!$I$6:$I$11,'Holgura'!$B$6:$B$11,$A8,'Holgura'!$E$6:$E$11,"Víctor")+SUMIFS('Holgura'!$I$6:$I$11,'Holgura'!$B$6:$B$11,$A8,'Holgura'!$E$6:$E$11,"Ambos")+SUMIFS('Entrega'!$I$6:$I$9,'Entrega'!$B$6:$B$9,$A8,'Entrega'!$E$6:$E$9,"Víctor")+SUMIFS('Entrega'!$I$6:$I$9,'Entrega'!$B$6:$B$9,$A8,'Entrega'!$E$6:$E$9,"Ambos")+SUMIFS('Defensa'!$I$6:$I$10,'Defensa'!$B$6:$B$10,$A8,'Defensa'!$E$6:$E$10,"Víctor")+SUMIFS('Defensa'!$I$6:$I$10,'Defensa'!$B$6:$B$10,$A8,'Defensa'!$E$6:$E$10,"Ambos")</f>
         <v/>
       </c>
       <c r="E8" s="21">
-        <f>SUMIFS('S1'!$I$6:$I$32,'S1'!$B$6:$B$32,$A8,'S1'!$E$6:$E$32,"Diego")+SUMIFS('S1'!$I$6:$I$32,'S1'!$B$6:$B$32,$A8,'S1'!$E$6:$E$32,"Ambos")+SUMIFS('S2'!$I$6:$I$23,'S2'!$B$6:$B$23,$A8,'S2'!$E$6:$E$23,"Diego")+SUMIFS('S2'!$I$6:$I$23,'S2'!$B$6:$B$23,$A8,'S2'!$E$6:$E$23,"Ambos")+SUMIFS('S3'!$I$6:$I$19,'S3'!$B$6:$B$19,$A8,'S3'!$E$6:$E$19,"Diego")+SUMIFS('S3'!$I$6:$I$19,'S3'!$B$6:$B$19,$A8,'S3'!$E$6:$E$19,"Ambos")+SUMIFS('S4'!$I$6:$I$20,'S4'!$B$6:$B$20,$A8,'S4'!$E$6:$E$20,"Diego")+SUMIFS('S4'!$I$6:$I$20,'S4'!$B$6:$B$20,$A8,'S4'!$E$6:$E$20,"Ambos")+SUMIFS('S5'!$I$6:$I$20,'S5'!$B$6:$B$20,$A8,'S5'!$E$6:$E$20,"Diego")+SUMIFS('S5'!$I$6:$I$20,'S5'!$B$6:$B$20,$A8,'S5'!$E$6:$E$20,"Ambos")+SUMIFS('S6'!$I$6:$I$17,'S6'!$B$6:$B$17,$A8,'S6'!$E$6:$E$17,"Diego")+SUMIFS('S6'!$I$6:$I$17,'S6'!$B$6:$B$17,$A8,'S6'!$E$6:$E$17,"Ambos")+SUMIFS('S7'!$I$6:$I$19,'S7'!$B$6:$B$19,$A8,'S7'!$E$6:$E$19,"Diego")+SUMIFS('S7'!$I$6:$I$19,'S7'!$B$6:$B$19,$A8,'S7'!$E$6:$E$19,"Ambos")+SUMIFS('S8'!$I$6:$I$23,'S8'!$B$6:$B$23,$A8,'S8'!$E$6:$E$23,"Diego")+SUMIFS('S8'!$I$6:$I$23,'S8'!$B$6:$B$23,$A8,'S8'!$E$6:$E$23,"Ambos")+SUMIFS('S9'!$I$6:$I$15,'S9'!$B$6:$B$15,$A8,'S9'!$E$6:$E$15,"Diego")+SUMIFS('S9'!$I$6:$I$15,'S9'!$B$6:$B$15,$A8,'S9'!$E$6:$E$15,"Ambos")+SUMIFS('S10'!$I$6:$I$13,'S10'!$B$6:$B$13,$A8,'S10'!$E$6:$E$13,"Diego")+SUMIFS('S10'!$I$6:$I$13,'S10'!$B$6:$B$13,$A8,'S10'!$E$6:$E$13,"Ambos")+SUMIFS('Holgura'!$I$6:$I$11,'Holgura'!$B$6:$B$11,$A8,'Holgura'!$E$6:$E$11,"Diego")+SUMIFS('Holgura'!$I$6:$I$11,'Holgura'!$B$6:$B$11,$A8,'Holgura'!$E$6:$E$11,"Ambos")+SUMIFS('Entrega'!$I$6:$I$9,'Entrega'!$B$6:$B$9,$A8,'Entrega'!$E$6:$E$9,"Diego")+SUMIFS('Entrega'!$I$6:$I$9,'Entrega'!$B$6:$B$9,$A8,'Entrega'!$E$6:$E$9,"Ambos")+SUMIFS('Defensa'!$I$6:$I$10,'Defensa'!$B$6:$B$10,$A8,'Defensa'!$E$6:$E$10,"Diego")+SUMIFS('Defensa'!$I$6:$I$10,'Defensa'!$B$6:$B$10,$A8,'Defensa'!$E$6:$E$10,"Ambos")</f>
+        <f>SUMIFS('S1'!$I$6:$I$32,'S1'!$B$6:$B$32,$A8,'S1'!$E$6:$E$32,"Diego")+SUMIFS('S1'!$I$6:$I$32,'S1'!$B$6:$B$32,$A8,'S1'!$E$6:$E$32,"Ambos")+SUMIFS('S2'!$I$6:$I$23,'S2'!$B$6:$B$23,$A8,'S2'!$E$6:$E$23,"Diego")+SUMIFS('S2'!$I$6:$I$23,'S2'!$B$6:$B$23,$A8,'S2'!$E$6:$E$23,"Ambos")+SUMIFS('S3'!$I$6:$I$24,'S3'!$B$6:$B$24,$A8,'S3'!$E$6:$E$24,"Diego")+SUMIFS('S3'!$I$6:$I$24,'S3'!$B$6:$B$24,$A8,'S3'!$E$6:$E$24,"Ambos")+SUMIFS('S4'!$I$6:$I$22,'S4'!$B$6:$B$22,$A8,'S4'!$E$6:$E$22,"Diego")+SUMIFS('S4'!$I$6:$I$22,'S4'!$B$6:$B$22,$A8,'S4'!$E$6:$E$22,"Ambos")+SUMIFS('S5'!$I$6:$I$20,'S5'!$B$6:$B$20,$A8,'S5'!$E$6:$E$20,"Diego")+SUMIFS('S5'!$I$6:$I$20,'S5'!$B$6:$B$20,$A8,'S5'!$E$6:$E$20,"Ambos")+SUMIFS('S6'!$I$6:$I$17,'S6'!$B$6:$B$17,$A8,'S6'!$E$6:$E$17,"Diego")+SUMIFS('S6'!$I$6:$I$17,'S6'!$B$6:$B$17,$A8,'S6'!$E$6:$E$17,"Ambos")+SUMIFS('S7'!$I$6:$I$19,'S7'!$B$6:$B$19,$A8,'S7'!$E$6:$E$19,"Diego")+SUMIFS('S7'!$I$6:$I$19,'S7'!$B$6:$B$19,$A8,'S7'!$E$6:$E$19,"Ambos")+SUMIFS('S8'!$I$6:$I$23,'S8'!$B$6:$B$23,$A8,'S8'!$E$6:$E$23,"Diego")+SUMIFS('S8'!$I$6:$I$23,'S8'!$B$6:$B$23,$A8,'S8'!$E$6:$E$23,"Ambos")+SUMIFS('S9'!$I$6:$I$15,'S9'!$B$6:$B$15,$A8,'S9'!$E$6:$E$15,"Diego")+SUMIFS('S9'!$I$6:$I$15,'S9'!$B$6:$B$15,$A8,'S9'!$E$6:$E$15,"Ambos")+SUMIFS('S10'!$I$6:$I$13,'S10'!$B$6:$B$13,$A8,'S10'!$E$6:$E$13,"Diego")+SUMIFS('S10'!$I$6:$I$13,'S10'!$B$6:$B$13,$A8,'S10'!$E$6:$E$13,"Ambos")+SUMIFS('Holgura'!$I$6:$I$11,'Holgura'!$B$6:$B$11,$A8,'Holgura'!$E$6:$E$11,"Diego")+SUMIFS('Holgura'!$I$6:$I$11,'Holgura'!$B$6:$B$11,$A8,'Holgura'!$E$6:$E$11,"Ambos")+SUMIFS('Entrega'!$I$6:$I$9,'Entrega'!$B$6:$B$9,$A8,'Entrega'!$E$6:$E$9,"Diego")+SUMIFS('Entrega'!$I$6:$I$9,'Entrega'!$B$6:$B$9,$A8,'Entrega'!$E$6:$E$9,"Ambos")+SUMIFS('Defensa'!$I$6:$I$10,'Defensa'!$B$6:$B$10,$A8,'Defensa'!$E$6:$E$10,"Diego")+SUMIFS('Defensa'!$I$6:$I$10,'Defensa'!$B$6:$B$10,$A8,'Defensa'!$E$6:$E$10,"Ambos")</f>
         <v/>
       </c>
       <c r="F8" s="21">
-        <f>COUNTIFS('S1'!$B$6:$B$32,$A8,'S1'!$E$6:$E$32,"Víctor")+COUNTIFS('S1'!$B$6:$B$32,$A8,'S1'!$E$6:$E$32,"Ambos")+COUNTIFS('S2'!$B$6:$B$23,$A8,'S2'!$E$6:$E$23,"Víctor")+COUNTIFS('S2'!$B$6:$B$23,$A8,'S2'!$E$6:$E$23,"Ambos")+COUNTIFS('S3'!$B$6:$B$19,$A8,'S3'!$E$6:$E$19,"Víctor")+COUNTIFS('S3'!$B$6:$B$19,$A8,'S3'!$E$6:$E$19,"Ambos")+COUNTIFS('S4'!$B$6:$B$20,$A8,'S4'!$E$6:$E$20,"Víctor")+COUNTIFS('S4'!$B$6:$B$20,$A8,'S4'!$E$6:$E$20,"Ambos")+COUNTIFS('S5'!$B$6:$B$20,$A8,'S5'!$E$6:$E$20,"Víctor")+COUNTIFS('S5'!$B$6:$B$20,$A8,'S5'!$E$6:$E$20,"Ambos")+COUNTIFS('S6'!$B$6:$B$17,$A8,'S6'!$E$6:$E$17,"Víctor")+COUNTIFS('S6'!$B$6:$B$17,$A8,'S6'!$E$6:$E$17,"Ambos")+COUNTIFS('S7'!$B$6:$B$19,$A8,'S7'!$E$6:$E$19,"Víctor")+COUNTIFS('S7'!$B$6:$B$19,$A8,'S7'!$E$6:$E$19,"Ambos")+COUNTIFS('S8'!$B$6:$B$23,$A8,'S8'!$E$6:$E$23,"Víctor")+COUNTIFS('S8'!$B$6:$B$23,$A8,'S8'!$E$6:$E$23,"Ambos")+COUNTIFS('S9'!$B$6:$B$15,$A8,'S9'!$E$6:$E$15,"Víctor")+COUNTIFS('S9'!$B$6:$B$15,$A8,'S9'!$E$6:$E$15,"Ambos")+COUNTIFS('S10'!$B$6:$B$13,$A8,'S10'!$E$6:$E$13,"Víctor")+COUNTIFS('S10'!$B$6:$B$13,$A8,'S10'!$E$6:$E$13,"Ambos")+COUNTIFS('Holgura'!$B$6:$B$11,$A8,'Holgura'!$E$6:$E$11,"Víctor")+COUNTIFS('Holgura'!$B$6:$B$11,$A8,'Holgura'!$E$6:$E$11,"Ambos")+COUNTIFS('Entrega'!$B$6:$B$9,$A8,'Entrega'!$E$6:$E$9,"Víctor")+COUNTIFS('Entrega'!$B$6:$B$9,$A8,'Entrega'!$E$6:$E$9,"Ambos")+COUNTIFS('Defensa'!$B$6:$B$10,$A8,'Defensa'!$E$6:$E$10,"Víctor")+COUNTIFS('Defensa'!$B$6:$B$10,$A8,'Defensa'!$E$6:$E$10,"Ambos")</f>
+        <f>COUNTIFS('S1'!$B$6:$B$32,$A8,'S1'!$E$6:$E$32,"Víctor")+COUNTIFS('S1'!$B$6:$B$32,$A8,'S1'!$E$6:$E$32,"Ambos")+COUNTIFS('S2'!$B$6:$B$23,$A8,'S2'!$E$6:$E$23,"Víctor")+COUNTIFS('S2'!$B$6:$B$23,$A8,'S2'!$E$6:$E$23,"Ambos")+COUNTIFS('S3'!$B$6:$B$24,$A8,'S3'!$E$6:$E$24,"Víctor")+COUNTIFS('S3'!$B$6:$B$24,$A8,'S3'!$E$6:$E$24,"Ambos")+COUNTIFS('S4'!$B$6:$B$22,$A8,'S4'!$E$6:$E$22,"Víctor")+COUNTIFS('S4'!$B$6:$B$22,$A8,'S4'!$E$6:$E$22,"Ambos")+COUNTIFS('S5'!$B$6:$B$20,$A8,'S5'!$E$6:$E$20,"Víctor")+COUNTIFS('S5'!$B$6:$B$20,$A8,'S5'!$E$6:$E$20,"Ambos")+COUNTIFS('S6'!$B$6:$B$17,$A8,'S6'!$E$6:$E$17,"Víctor")+COUNTIFS('S6'!$B$6:$B$17,$A8,'S6'!$E$6:$E$17,"Ambos")+COUNTIFS('S7'!$B$6:$B$19,$A8,'S7'!$E$6:$E$19,"Víctor")+COUNTIFS('S7'!$B$6:$B$19,$A8,'S7'!$E$6:$E$19,"Ambos")+COUNTIFS('S8'!$B$6:$B$23,$A8,'S8'!$E$6:$E$23,"Víctor")+COUNTIFS('S8'!$B$6:$B$23,$A8,'S8'!$E$6:$E$23,"Ambos")+COUNTIFS('S9'!$B$6:$B$15,$A8,'S9'!$E$6:$E$15,"Víctor")+COUNTIFS('S9'!$B$6:$B$15,$A8,'S9'!$E$6:$E$15,"Ambos")+COUNTIFS('S10'!$B$6:$B$13,$A8,'S10'!$E$6:$E$13,"Víctor")+COUNTIFS('S10'!$B$6:$B$13,$A8,'S10'!$E$6:$E$13,"Ambos")+COUNTIFS('Holgura'!$B$6:$B$11,$A8,'Holgura'!$E$6:$E$11,"Víctor")+COUNTIFS('Holgura'!$B$6:$B$11,$A8,'Holgura'!$E$6:$E$11,"Ambos")+COUNTIFS('Entrega'!$B$6:$B$9,$A8,'Entrega'!$E$6:$E$9,"Víctor")+COUNTIFS('Entrega'!$B$6:$B$9,$A8,'Entrega'!$E$6:$E$9,"Ambos")+COUNTIFS('Defensa'!$B$6:$B$10,$A8,'Defensa'!$E$6:$E$10,"Víctor")+COUNTIFS('Defensa'!$B$6:$B$10,$A8,'Defensa'!$E$6:$E$10,"Ambos")</f>
         <v/>
       </c>
       <c r="G8" s="21">
-        <f>COUNTIFS('S1'!$B$6:$B$32,$A8,'S1'!$E$6:$E$32,"Diego")+COUNTIFS('S1'!$B$6:$B$32,$A8,'S1'!$E$6:$E$32,"Ambos")+COUNTIFS('S2'!$B$6:$B$23,$A8,'S2'!$E$6:$E$23,"Diego")+COUNTIFS('S2'!$B$6:$B$23,$A8,'S2'!$E$6:$E$23,"Ambos")+COUNTIFS('S3'!$B$6:$B$19,$A8,'S3'!$E$6:$E$19,"Diego")+COUNTIFS('S3'!$B$6:$B$19,$A8,'S3'!$E$6:$E$19,"Ambos")+COUNTIFS('S4'!$B$6:$B$20,$A8,'S4'!$E$6:$E$20,"Diego")+COUNTIFS('S4'!$B$6:$B$20,$A8,'S4'!$E$6:$E$20,"Ambos")+COUNTIFS('S5'!$B$6:$B$20,$A8,'S5'!$E$6:$E$20,"Diego")+COUNTIFS('S5'!$B$6:$B$20,$A8,'S5'!$E$6:$E$20,"Ambos")+COUNTIFS('S6'!$B$6:$B$17,$A8,'S6'!$E$6:$E$17,"Diego")+COUNTIFS('S6'!$B$6:$B$17,$A8,'S6'!$E$6:$E$17,"Ambos")+COUNTIFS('S7'!$B$6:$B$19,$A8,'S7'!$E$6:$E$19,"Diego")+COUNTIFS('S7'!$B$6:$B$19,$A8,'S7'!$E$6:$E$19,"Ambos")+COUNTIFS('S8'!$B$6:$B$23,$A8,'S8'!$E$6:$E$23,"Diego")+COUNTIFS('S8'!$B$6:$B$23,$A8,'S8'!$E$6:$E$23,"Ambos")+COUNTIFS('S9'!$B$6:$B$15,$A8,'S9'!$E$6:$E$15,"Diego")+COUNTIFS('S9'!$B$6:$B$15,$A8,'S9'!$E$6:$E$15,"Ambos")+COUNTIFS('S10'!$B$6:$B$13,$A8,'S10'!$E$6:$E$13,"Diego")+COUNTIFS('S10'!$B$6:$B$13,$A8,'S10'!$E$6:$E$13,"Ambos")+COUNTIFS('Holgura'!$B$6:$B$11,$A8,'Holgura'!$E$6:$E$11,"Diego")+COUNTIFS('Holgura'!$B$6:$B$11,$A8,'Holgura'!$E$6:$E$11,"Ambos")+COUNTIFS('Entrega'!$B$6:$B$9,$A8,'Entrega'!$E$6:$E$9,"Diego")+COUNTIFS('Entrega'!$B$6:$B$9,$A8,'Entrega'!$E$6:$E$9,"Ambos")+COUNTIFS('Defensa'!$B$6:$B$10,$A8,'Defensa'!$E$6:$E$10,"Diego")+COUNTIFS('Defensa'!$B$6:$B$10,$A8,'Defensa'!$E$6:$E$10,"Ambos")</f>
+        <f>COUNTIFS('S1'!$B$6:$B$32,$A8,'S1'!$E$6:$E$32,"Diego")+COUNTIFS('S1'!$B$6:$B$32,$A8,'S1'!$E$6:$E$32,"Ambos")+COUNTIFS('S2'!$B$6:$B$23,$A8,'S2'!$E$6:$E$23,"Diego")+COUNTIFS('S2'!$B$6:$B$23,$A8,'S2'!$E$6:$E$23,"Ambos")+COUNTIFS('S3'!$B$6:$B$24,$A8,'S3'!$E$6:$E$24,"Diego")+COUNTIFS('S3'!$B$6:$B$24,$A8,'S3'!$E$6:$E$24,"Ambos")+COUNTIFS('S4'!$B$6:$B$22,$A8,'S4'!$E$6:$E$22,"Diego")+COUNTIFS('S4'!$B$6:$B$22,$A8,'S4'!$E$6:$E$22,"Ambos")+COUNTIFS('S5'!$B$6:$B$20,$A8,'S5'!$E$6:$E$20,"Diego")+COUNTIFS('S5'!$B$6:$B$20,$A8,'S5'!$E$6:$E$20,"Ambos")+COUNTIFS('S6'!$B$6:$B$17,$A8,'S6'!$E$6:$E$17,"Diego")+COUNTIFS('S6'!$B$6:$B$17,$A8,'S6'!$E$6:$E$17,"Ambos")+COUNTIFS('S7'!$B$6:$B$19,$A8,'S7'!$E$6:$E$19,"Diego")+COUNTIFS('S7'!$B$6:$B$19,$A8,'S7'!$E$6:$E$19,"Ambos")+COUNTIFS('S8'!$B$6:$B$23,$A8,'S8'!$E$6:$E$23,"Diego")+COUNTIFS('S8'!$B$6:$B$23,$A8,'S8'!$E$6:$E$23,"Ambos")+COUNTIFS('S9'!$B$6:$B$15,$A8,'S9'!$E$6:$E$15,"Diego")+COUNTIFS('S9'!$B$6:$B$15,$A8,'S9'!$E$6:$E$15,"Ambos")+COUNTIFS('S10'!$B$6:$B$13,$A8,'S10'!$E$6:$E$13,"Diego")+COUNTIFS('S10'!$B$6:$B$13,$A8,'S10'!$E$6:$E$13,"Ambos")+COUNTIFS('Holgura'!$B$6:$B$11,$A8,'Holgura'!$E$6:$E$11,"Diego")+COUNTIFS('Holgura'!$B$6:$B$11,$A8,'Holgura'!$E$6:$E$11,"Ambos")+COUNTIFS('Entrega'!$B$6:$B$9,$A8,'Entrega'!$E$6:$E$9,"Diego")+COUNTIFS('Entrega'!$B$6:$B$9,$A8,'Entrega'!$E$6:$E$9,"Ambos")+COUNTIFS('Defensa'!$B$6:$B$10,$A8,'Defensa'!$E$6:$E$10,"Diego")+COUNTIFS('Defensa'!$B$6:$B$10,$A8,'Defensa'!$E$6:$E$10,"Ambos")</f>
         <v/>
       </c>
     </row>
@@ -8796,19 +8817,19 @@
         <v/>
       </c>
       <c r="D9" s="21">
-        <f>SUMIFS('S1'!$I$6:$I$32,'S1'!$B$6:$B$32,$A9,'S1'!$E$6:$E$32,"Víctor")+SUMIFS('S1'!$I$6:$I$32,'S1'!$B$6:$B$32,$A9,'S1'!$E$6:$E$32,"Ambos")+SUMIFS('S2'!$I$6:$I$23,'S2'!$B$6:$B$23,$A9,'S2'!$E$6:$E$23,"Víctor")+SUMIFS('S2'!$I$6:$I$23,'S2'!$B$6:$B$23,$A9,'S2'!$E$6:$E$23,"Ambos")+SUMIFS('S3'!$I$6:$I$19,'S3'!$B$6:$B$19,$A9,'S3'!$E$6:$E$19,"Víctor")+SUMIFS('S3'!$I$6:$I$19,'S3'!$B$6:$B$19,$A9,'S3'!$E$6:$E$19,"Ambos")+SUMIFS('S4'!$I$6:$I$20,'S4'!$B$6:$B$20,$A9,'S4'!$E$6:$E$20,"Víctor")+SUMIFS('S4'!$I$6:$I$20,'S4'!$B$6:$B$20,$A9,'S4'!$E$6:$E$20,"Ambos")+SUMIFS('S5'!$I$6:$I$20,'S5'!$B$6:$B$20,$A9,'S5'!$E$6:$E$20,"Víctor")+SUMIFS('S5'!$I$6:$I$20,'S5'!$B$6:$B$20,$A9,'S5'!$E$6:$E$20,"Ambos")+SUMIFS('S6'!$I$6:$I$17,'S6'!$B$6:$B$17,$A9,'S6'!$E$6:$E$17,"Víctor")+SUMIFS('S6'!$I$6:$I$17,'S6'!$B$6:$B$17,$A9,'S6'!$E$6:$E$17,"Ambos")+SUMIFS('S7'!$I$6:$I$19,'S7'!$B$6:$B$19,$A9,'S7'!$E$6:$E$19,"Víctor")+SUMIFS('S7'!$I$6:$I$19,'S7'!$B$6:$B$19,$A9,'S7'!$E$6:$E$19,"Ambos")+SUMIFS('S8'!$I$6:$I$23,'S8'!$B$6:$B$23,$A9,'S8'!$E$6:$E$23,"Víctor")+SUMIFS('S8'!$I$6:$I$23,'S8'!$B$6:$B$23,$A9,'S8'!$E$6:$E$23,"Ambos")+SUMIFS('S9'!$I$6:$I$15,'S9'!$B$6:$B$15,$A9,'S9'!$E$6:$E$15,"Víctor")+SUMIFS('S9'!$I$6:$I$15,'S9'!$B$6:$B$15,$A9,'S9'!$E$6:$E$15,"Ambos")+SUMIFS('S10'!$I$6:$I$13,'S10'!$B$6:$B$13,$A9,'S10'!$E$6:$E$13,"Víctor")+SUMIFS('S10'!$I$6:$I$13,'S10'!$B$6:$B$13,$A9,'S10'!$E$6:$E$13,"Ambos")+SUMIFS('Holgura'!$I$6:$I$11,'Holgura'!$B$6:$B$11,$A9,'Holgura'!$E$6:$E$11,"Víctor")+SUMIFS('Holgura'!$I$6:$I$11,'Holgura'!$B$6:$B$11,$A9,'Holgura'!$E$6:$E$11,"Ambos")+SUMIFS('Entrega'!$I$6:$I$9,'Entrega'!$B$6:$B$9,$A9,'Entrega'!$E$6:$E$9,"Víctor")+SUMIFS('Entrega'!$I$6:$I$9,'Entrega'!$B$6:$B$9,$A9,'Entrega'!$E$6:$E$9,"Ambos")+SUMIFS('Defensa'!$I$6:$I$10,'Defensa'!$B$6:$B$10,$A9,'Defensa'!$E$6:$E$10,"Víctor")+SUMIFS('Defensa'!$I$6:$I$10,'Defensa'!$B$6:$B$10,$A9,'Defensa'!$E$6:$E$10,"Ambos")</f>
+        <f>SUMIFS('S1'!$I$6:$I$32,'S1'!$B$6:$B$32,$A9,'S1'!$E$6:$E$32,"Víctor")+SUMIFS('S1'!$I$6:$I$32,'S1'!$B$6:$B$32,$A9,'S1'!$E$6:$E$32,"Ambos")+SUMIFS('S2'!$I$6:$I$23,'S2'!$B$6:$B$23,$A9,'S2'!$E$6:$E$23,"Víctor")+SUMIFS('S2'!$I$6:$I$23,'S2'!$B$6:$B$23,$A9,'S2'!$E$6:$E$23,"Ambos")+SUMIFS('S3'!$I$6:$I$24,'S3'!$B$6:$B$24,$A9,'S3'!$E$6:$E$24,"Víctor")+SUMIFS('S3'!$I$6:$I$24,'S3'!$B$6:$B$24,$A9,'S3'!$E$6:$E$24,"Ambos")+SUMIFS('S4'!$I$6:$I$22,'S4'!$B$6:$B$22,$A9,'S4'!$E$6:$E$22,"Víctor")+SUMIFS('S4'!$I$6:$I$22,'S4'!$B$6:$B$22,$A9,'S4'!$E$6:$E$22,"Ambos")+SUMIFS('S5'!$I$6:$I$20,'S5'!$B$6:$B$20,$A9,'S5'!$E$6:$E$20,"Víctor")+SUMIFS('S5'!$I$6:$I$20,'S5'!$B$6:$B$20,$A9,'S5'!$E$6:$E$20,"Ambos")+SUMIFS('S6'!$I$6:$I$17,'S6'!$B$6:$B$17,$A9,'S6'!$E$6:$E$17,"Víctor")+SUMIFS('S6'!$I$6:$I$17,'S6'!$B$6:$B$17,$A9,'S6'!$E$6:$E$17,"Ambos")+SUMIFS('S7'!$I$6:$I$19,'S7'!$B$6:$B$19,$A9,'S7'!$E$6:$E$19,"Víctor")+SUMIFS('S7'!$I$6:$I$19,'S7'!$B$6:$B$19,$A9,'S7'!$E$6:$E$19,"Ambos")+SUMIFS('S8'!$I$6:$I$23,'S8'!$B$6:$B$23,$A9,'S8'!$E$6:$E$23,"Víctor")+SUMIFS('S8'!$I$6:$I$23,'S8'!$B$6:$B$23,$A9,'S8'!$E$6:$E$23,"Ambos")+SUMIFS('S9'!$I$6:$I$15,'S9'!$B$6:$B$15,$A9,'S9'!$E$6:$E$15,"Víctor")+SUMIFS('S9'!$I$6:$I$15,'S9'!$B$6:$B$15,$A9,'S9'!$E$6:$E$15,"Ambos")+SUMIFS('S10'!$I$6:$I$13,'S10'!$B$6:$B$13,$A9,'S10'!$E$6:$E$13,"Víctor")+SUMIFS('S10'!$I$6:$I$13,'S10'!$B$6:$B$13,$A9,'S10'!$E$6:$E$13,"Ambos")+SUMIFS('Holgura'!$I$6:$I$11,'Holgura'!$B$6:$B$11,$A9,'Holgura'!$E$6:$E$11,"Víctor")+SUMIFS('Holgura'!$I$6:$I$11,'Holgura'!$B$6:$B$11,$A9,'Holgura'!$E$6:$E$11,"Ambos")+SUMIFS('Entrega'!$I$6:$I$9,'Entrega'!$B$6:$B$9,$A9,'Entrega'!$E$6:$E$9,"Víctor")+SUMIFS('Entrega'!$I$6:$I$9,'Entrega'!$B$6:$B$9,$A9,'Entrega'!$E$6:$E$9,"Ambos")+SUMIFS('Defensa'!$I$6:$I$10,'Defensa'!$B$6:$B$10,$A9,'Defensa'!$E$6:$E$10,"Víctor")+SUMIFS('Defensa'!$I$6:$I$10,'Defensa'!$B$6:$B$10,$A9,'Defensa'!$E$6:$E$10,"Ambos")</f>
         <v/>
       </c>
       <c r="E9" s="21">
-        <f>SUMIFS('S1'!$I$6:$I$32,'S1'!$B$6:$B$32,$A9,'S1'!$E$6:$E$32,"Diego")+SUMIFS('S1'!$I$6:$I$32,'S1'!$B$6:$B$32,$A9,'S1'!$E$6:$E$32,"Ambos")+SUMIFS('S2'!$I$6:$I$23,'S2'!$B$6:$B$23,$A9,'S2'!$E$6:$E$23,"Diego")+SUMIFS('S2'!$I$6:$I$23,'S2'!$B$6:$B$23,$A9,'S2'!$E$6:$E$23,"Ambos")+SUMIFS('S3'!$I$6:$I$19,'S3'!$B$6:$B$19,$A9,'S3'!$E$6:$E$19,"Diego")+SUMIFS('S3'!$I$6:$I$19,'S3'!$B$6:$B$19,$A9,'S3'!$E$6:$E$19,"Ambos")+SUMIFS('S4'!$I$6:$I$20,'S4'!$B$6:$B$20,$A9,'S4'!$E$6:$E$20,"Diego")+SUMIFS('S4'!$I$6:$I$20,'S4'!$B$6:$B$20,$A9,'S4'!$E$6:$E$20,"Ambos")+SUMIFS('S5'!$I$6:$I$20,'S5'!$B$6:$B$20,$A9,'S5'!$E$6:$E$20,"Diego")+SUMIFS('S5'!$I$6:$I$20,'S5'!$B$6:$B$20,$A9,'S5'!$E$6:$E$20,"Ambos")+SUMIFS('S6'!$I$6:$I$17,'S6'!$B$6:$B$17,$A9,'S6'!$E$6:$E$17,"Diego")+SUMIFS('S6'!$I$6:$I$17,'S6'!$B$6:$B$17,$A9,'S6'!$E$6:$E$17,"Ambos")+SUMIFS('S7'!$I$6:$I$19,'S7'!$B$6:$B$19,$A9,'S7'!$E$6:$E$19,"Diego")+SUMIFS('S7'!$I$6:$I$19,'S7'!$B$6:$B$19,$A9,'S7'!$E$6:$E$19,"Ambos")+SUMIFS('S8'!$I$6:$I$23,'S8'!$B$6:$B$23,$A9,'S8'!$E$6:$E$23,"Diego")+SUMIFS('S8'!$I$6:$I$23,'S8'!$B$6:$B$23,$A9,'S8'!$E$6:$E$23,"Ambos")+SUMIFS('S9'!$I$6:$I$15,'S9'!$B$6:$B$15,$A9,'S9'!$E$6:$E$15,"Diego")+SUMIFS('S9'!$I$6:$I$15,'S9'!$B$6:$B$15,$A9,'S9'!$E$6:$E$15,"Ambos")+SUMIFS('S10'!$I$6:$I$13,'S10'!$B$6:$B$13,$A9,'S10'!$E$6:$E$13,"Diego")+SUMIFS('S10'!$I$6:$I$13,'S10'!$B$6:$B$13,$A9,'S10'!$E$6:$E$13,"Ambos")+SUMIFS('Holgura'!$I$6:$I$11,'Holgura'!$B$6:$B$11,$A9,'Holgura'!$E$6:$E$11,"Diego")+SUMIFS('Holgura'!$I$6:$I$11,'Holgura'!$B$6:$B$11,$A9,'Holgura'!$E$6:$E$11,"Ambos")+SUMIFS('Entrega'!$I$6:$I$9,'Entrega'!$B$6:$B$9,$A9,'Entrega'!$E$6:$E$9,"Diego")+SUMIFS('Entrega'!$I$6:$I$9,'Entrega'!$B$6:$B$9,$A9,'Entrega'!$E$6:$E$9,"Ambos")+SUMIFS('Defensa'!$I$6:$I$10,'Defensa'!$B$6:$B$10,$A9,'Defensa'!$E$6:$E$10,"Diego")+SUMIFS('Defensa'!$I$6:$I$10,'Defensa'!$B$6:$B$10,$A9,'Defensa'!$E$6:$E$10,"Ambos")</f>
+        <f>SUMIFS('S1'!$I$6:$I$32,'S1'!$B$6:$B$32,$A9,'S1'!$E$6:$E$32,"Diego")+SUMIFS('S1'!$I$6:$I$32,'S1'!$B$6:$B$32,$A9,'S1'!$E$6:$E$32,"Ambos")+SUMIFS('S2'!$I$6:$I$23,'S2'!$B$6:$B$23,$A9,'S2'!$E$6:$E$23,"Diego")+SUMIFS('S2'!$I$6:$I$23,'S2'!$B$6:$B$23,$A9,'S2'!$E$6:$E$23,"Ambos")+SUMIFS('S3'!$I$6:$I$24,'S3'!$B$6:$B$24,$A9,'S3'!$E$6:$E$24,"Diego")+SUMIFS('S3'!$I$6:$I$24,'S3'!$B$6:$B$24,$A9,'S3'!$E$6:$E$24,"Ambos")+SUMIFS('S4'!$I$6:$I$22,'S4'!$B$6:$B$22,$A9,'S4'!$E$6:$E$22,"Diego")+SUMIFS('S4'!$I$6:$I$22,'S4'!$B$6:$B$22,$A9,'S4'!$E$6:$E$22,"Ambos")+SUMIFS('S5'!$I$6:$I$20,'S5'!$B$6:$B$20,$A9,'S5'!$E$6:$E$20,"Diego")+SUMIFS('S5'!$I$6:$I$20,'S5'!$B$6:$B$20,$A9,'S5'!$E$6:$E$20,"Ambos")+SUMIFS('S6'!$I$6:$I$17,'S6'!$B$6:$B$17,$A9,'S6'!$E$6:$E$17,"Diego")+SUMIFS('S6'!$I$6:$I$17,'S6'!$B$6:$B$17,$A9,'S6'!$E$6:$E$17,"Ambos")+SUMIFS('S7'!$I$6:$I$19,'S7'!$B$6:$B$19,$A9,'S7'!$E$6:$E$19,"Diego")+SUMIFS('S7'!$I$6:$I$19,'S7'!$B$6:$B$19,$A9,'S7'!$E$6:$E$19,"Ambos")+SUMIFS('S8'!$I$6:$I$23,'S8'!$B$6:$B$23,$A9,'S8'!$E$6:$E$23,"Diego")+SUMIFS('S8'!$I$6:$I$23,'S8'!$B$6:$B$23,$A9,'S8'!$E$6:$E$23,"Ambos")+SUMIFS('S9'!$I$6:$I$15,'S9'!$B$6:$B$15,$A9,'S9'!$E$6:$E$15,"Diego")+SUMIFS('S9'!$I$6:$I$15,'S9'!$B$6:$B$15,$A9,'S9'!$E$6:$E$15,"Ambos")+SUMIFS('S10'!$I$6:$I$13,'S10'!$B$6:$B$13,$A9,'S10'!$E$6:$E$13,"Diego")+SUMIFS('S10'!$I$6:$I$13,'S10'!$B$6:$B$13,$A9,'S10'!$E$6:$E$13,"Ambos")+SUMIFS('Holgura'!$I$6:$I$11,'Holgura'!$B$6:$B$11,$A9,'Holgura'!$E$6:$E$11,"Diego")+SUMIFS('Holgura'!$I$6:$I$11,'Holgura'!$B$6:$B$11,$A9,'Holgura'!$E$6:$E$11,"Ambos")+SUMIFS('Entrega'!$I$6:$I$9,'Entrega'!$B$6:$B$9,$A9,'Entrega'!$E$6:$E$9,"Diego")+SUMIFS('Entrega'!$I$6:$I$9,'Entrega'!$B$6:$B$9,$A9,'Entrega'!$E$6:$E$9,"Ambos")+SUMIFS('Defensa'!$I$6:$I$10,'Defensa'!$B$6:$B$10,$A9,'Defensa'!$E$6:$E$10,"Diego")+SUMIFS('Defensa'!$I$6:$I$10,'Defensa'!$B$6:$B$10,$A9,'Defensa'!$E$6:$E$10,"Ambos")</f>
         <v/>
       </c>
       <c r="F9" s="21">
-        <f>COUNTIFS('S1'!$B$6:$B$32,$A9,'S1'!$E$6:$E$32,"Víctor")+COUNTIFS('S1'!$B$6:$B$32,$A9,'S1'!$E$6:$E$32,"Ambos")+COUNTIFS('S2'!$B$6:$B$23,$A9,'S2'!$E$6:$E$23,"Víctor")+COUNTIFS('S2'!$B$6:$B$23,$A9,'S2'!$E$6:$E$23,"Ambos")+COUNTIFS('S3'!$B$6:$B$19,$A9,'S3'!$E$6:$E$19,"Víctor")+COUNTIFS('S3'!$B$6:$B$19,$A9,'S3'!$E$6:$E$19,"Ambos")+COUNTIFS('S4'!$B$6:$B$20,$A9,'S4'!$E$6:$E$20,"Víctor")+COUNTIFS('S4'!$B$6:$B$20,$A9,'S4'!$E$6:$E$20,"Ambos")+COUNTIFS('S5'!$B$6:$B$20,$A9,'S5'!$E$6:$E$20,"Víctor")+COUNTIFS('S5'!$B$6:$B$20,$A9,'S5'!$E$6:$E$20,"Ambos")+COUNTIFS('S6'!$B$6:$B$17,$A9,'S6'!$E$6:$E$17,"Víctor")+COUNTIFS('S6'!$B$6:$B$17,$A9,'S6'!$E$6:$E$17,"Ambos")+COUNTIFS('S7'!$B$6:$B$19,$A9,'S7'!$E$6:$E$19,"Víctor")+COUNTIFS('S7'!$B$6:$B$19,$A9,'S7'!$E$6:$E$19,"Ambos")+COUNTIFS('S8'!$B$6:$B$23,$A9,'S8'!$E$6:$E$23,"Víctor")+COUNTIFS('S8'!$B$6:$B$23,$A9,'S8'!$E$6:$E$23,"Ambos")+COUNTIFS('S9'!$B$6:$B$15,$A9,'S9'!$E$6:$E$15,"Víctor")+COUNTIFS('S9'!$B$6:$B$15,$A9,'S9'!$E$6:$E$15,"Ambos")+COUNTIFS('S10'!$B$6:$B$13,$A9,'S10'!$E$6:$E$13,"Víctor")+COUNTIFS('S10'!$B$6:$B$13,$A9,'S10'!$E$6:$E$13,"Ambos")+COUNTIFS('Holgura'!$B$6:$B$11,$A9,'Holgura'!$E$6:$E$11,"Víctor")+COUNTIFS('Holgura'!$B$6:$B$11,$A9,'Holgura'!$E$6:$E$11,"Ambos")+COUNTIFS('Entrega'!$B$6:$B$9,$A9,'Entrega'!$E$6:$E$9,"Víctor")+COUNTIFS('Entrega'!$B$6:$B$9,$A9,'Entrega'!$E$6:$E$9,"Ambos")+COUNTIFS('Defensa'!$B$6:$B$10,$A9,'Defensa'!$E$6:$E$10,"Víctor")+COUNTIFS('Defensa'!$B$6:$B$10,$A9,'Defensa'!$E$6:$E$10,"Ambos")</f>
+        <f>COUNTIFS('S1'!$B$6:$B$32,$A9,'S1'!$E$6:$E$32,"Víctor")+COUNTIFS('S1'!$B$6:$B$32,$A9,'S1'!$E$6:$E$32,"Ambos")+COUNTIFS('S2'!$B$6:$B$23,$A9,'S2'!$E$6:$E$23,"Víctor")+COUNTIFS('S2'!$B$6:$B$23,$A9,'S2'!$E$6:$E$23,"Ambos")+COUNTIFS('S3'!$B$6:$B$24,$A9,'S3'!$E$6:$E$24,"Víctor")+COUNTIFS('S3'!$B$6:$B$24,$A9,'S3'!$E$6:$E$24,"Ambos")+COUNTIFS('S4'!$B$6:$B$22,$A9,'S4'!$E$6:$E$22,"Víctor")+COUNTIFS('S4'!$B$6:$B$22,$A9,'S4'!$E$6:$E$22,"Ambos")+COUNTIFS('S5'!$B$6:$B$20,$A9,'S5'!$E$6:$E$20,"Víctor")+COUNTIFS('S5'!$B$6:$B$20,$A9,'S5'!$E$6:$E$20,"Ambos")+COUNTIFS('S6'!$B$6:$B$17,$A9,'S6'!$E$6:$E$17,"Víctor")+COUNTIFS('S6'!$B$6:$B$17,$A9,'S6'!$E$6:$E$17,"Ambos")+COUNTIFS('S7'!$B$6:$B$19,$A9,'S7'!$E$6:$E$19,"Víctor")+COUNTIFS('S7'!$B$6:$B$19,$A9,'S7'!$E$6:$E$19,"Ambos")+COUNTIFS('S8'!$B$6:$B$23,$A9,'S8'!$E$6:$E$23,"Víctor")+COUNTIFS('S8'!$B$6:$B$23,$A9,'S8'!$E$6:$E$23,"Ambos")+COUNTIFS('S9'!$B$6:$B$15,$A9,'S9'!$E$6:$E$15,"Víctor")+COUNTIFS('S9'!$B$6:$B$15,$A9,'S9'!$E$6:$E$15,"Ambos")+COUNTIFS('S10'!$B$6:$B$13,$A9,'S10'!$E$6:$E$13,"Víctor")+COUNTIFS('S10'!$B$6:$B$13,$A9,'S10'!$E$6:$E$13,"Ambos")+COUNTIFS('Holgura'!$B$6:$B$11,$A9,'Holgura'!$E$6:$E$11,"Víctor")+COUNTIFS('Holgura'!$B$6:$B$11,$A9,'Holgura'!$E$6:$E$11,"Ambos")+COUNTIFS('Entrega'!$B$6:$B$9,$A9,'Entrega'!$E$6:$E$9,"Víctor")+COUNTIFS('Entrega'!$B$6:$B$9,$A9,'Entrega'!$E$6:$E$9,"Ambos")+COUNTIFS('Defensa'!$B$6:$B$10,$A9,'Defensa'!$E$6:$E$10,"Víctor")+COUNTIFS('Defensa'!$B$6:$B$10,$A9,'Defensa'!$E$6:$E$10,"Ambos")</f>
         <v/>
       </c>
       <c r="G9" s="21">
-        <f>COUNTIFS('S1'!$B$6:$B$32,$A9,'S1'!$E$6:$E$32,"Diego")+COUNTIFS('S1'!$B$6:$B$32,$A9,'S1'!$E$6:$E$32,"Ambos")+COUNTIFS('S2'!$B$6:$B$23,$A9,'S2'!$E$6:$E$23,"Diego")+COUNTIFS('S2'!$B$6:$B$23,$A9,'S2'!$E$6:$E$23,"Ambos")+COUNTIFS('S3'!$B$6:$B$19,$A9,'S3'!$E$6:$E$19,"Diego")+COUNTIFS('S3'!$B$6:$B$19,$A9,'S3'!$E$6:$E$19,"Ambos")+COUNTIFS('S4'!$B$6:$B$20,$A9,'S4'!$E$6:$E$20,"Diego")+COUNTIFS('S4'!$B$6:$B$20,$A9,'S4'!$E$6:$E$20,"Ambos")+COUNTIFS('S5'!$B$6:$B$20,$A9,'S5'!$E$6:$E$20,"Diego")+COUNTIFS('S5'!$B$6:$B$20,$A9,'S5'!$E$6:$E$20,"Ambos")+COUNTIFS('S6'!$B$6:$B$17,$A9,'S6'!$E$6:$E$17,"Diego")+COUNTIFS('S6'!$B$6:$B$17,$A9,'S6'!$E$6:$E$17,"Ambos")+COUNTIFS('S7'!$B$6:$B$19,$A9,'S7'!$E$6:$E$19,"Diego")+COUNTIFS('S7'!$B$6:$B$19,$A9,'S7'!$E$6:$E$19,"Ambos")+COUNTIFS('S8'!$B$6:$B$23,$A9,'S8'!$E$6:$E$23,"Diego")+COUNTIFS('S8'!$B$6:$B$23,$A9,'S8'!$E$6:$E$23,"Ambos")+COUNTIFS('S9'!$B$6:$B$15,$A9,'S9'!$E$6:$E$15,"Diego")+COUNTIFS('S9'!$B$6:$B$15,$A9,'S9'!$E$6:$E$15,"Ambos")+COUNTIFS('S10'!$B$6:$B$13,$A9,'S10'!$E$6:$E$13,"Diego")+COUNTIFS('S10'!$B$6:$B$13,$A9,'S10'!$E$6:$E$13,"Ambos")+COUNTIFS('Holgura'!$B$6:$B$11,$A9,'Holgura'!$E$6:$E$11,"Diego")+COUNTIFS('Holgura'!$B$6:$B$11,$A9,'Holgura'!$E$6:$E$11,"Ambos")+COUNTIFS('Entrega'!$B$6:$B$9,$A9,'Entrega'!$E$6:$E$9,"Diego")+COUNTIFS('Entrega'!$B$6:$B$9,$A9,'Entrega'!$E$6:$E$9,"Ambos")+COUNTIFS('Defensa'!$B$6:$B$10,$A9,'Defensa'!$E$6:$E$10,"Diego")+COUNTIFS('Defensa'!$B$6:$B$10,$A9,'Defensa'!$E$6:$E$10,"Ambos")</f>
+        <f>COUNTIFS('S1'!$B$6:$B$32,$A9,'S1'!$E$6:$E$32,"Diego")+COUNTIFS('S1'!$B$6:$B$32,$A9,'S1'!$E$6:$E$32,"Ambos")+COUNTIFS('S2'!$B$6:$B$23,$A9,'S2'!$E$6:$E$23,"Diego")+COUNTIFS('S2'!$B$6:$B$23,$A9,'S2'!$E$6:$E$23,"Ambos")+COUNTIFS('S3'!$B$6:$B$24,$A9,'S3'!$E$6:$E$24,"Diego")+COUNTIFS('S3'!$B$6:$B$24,$A9,'S3'!$E$6:$E$24,"Ambos")+COUNTIFS('S4'!$B$6:$B$22,$A9,'S4'!$E$6:$E$22,"Diego")+COUNTIFS('S4'!$B$6:$B$22,$A9,'S4'!$E$6:$E$22,"Ambos")+COUNTIFS('S5'!$B$6:$B$20,$A9,'S5'!$E$6:$E$20,"Diego")+COUNTIFS('S5'!$B$6:$B$20,$A9,'S5'!$E$6:$E$20,"Ambos")+COUNTIFS('S6'!$B$6:$B$17,$A9,'S6'!$E$6:$E$17,"Diego")+COUNTIFS('S6'!$B$6:$B$17,$A9,'S6'!$E$6:$E$17,"Ambos")+COUNTIFS('S7'!$B$6:$B$19,$A9,'S7'!$E$6:$E$19,"Diego")+COUNTIFS('S7'!$B$6:$B$19,$A9,'S7'!$E$6:$E$19,"Ambos")+COUNTIFS('S8'!$B$6:$B$23,$A9,'S8'!$E$6:$E$23,"Diego")+COUNTIFS('S8'!$B$6:$B$23,$A9,'S8'!$E$6:$E$23,"Ambos")+COUNTIFS('S9'!$B$6:$B$15,$A9,'S9'!$E$6:$E$15,"Diego")+COUNTIFS('S9'!$B$6:$B$15,$A9,'S9'!$E$6:$E$15,"Ambos")+COUNTIFS('S10'!$B$6:$B$13,$A9,'S10'!$E$6:$E$13,"Diego")+COUNTIFS('S10'!$B$6:$B$13,$A9,'S10'!$E$6:$E$13,"Ambos")+COUNTIFS('Holgura'!$B$6:$B$11,$A9,'Holgura'!$E$6:$E$11,"Diego")+COUNTIFS('Holgura'!$B$6:$B$11,$A9,'Holgura'!$E$6:$E$11,"Ambos")+COUNTIFS('Entrega'!$B$6:$B$9,$A9,'Entrega'!$E$6:$E$9,"Diego")+COUNTIFS('Entrega'!$B$6:$B$9,$A9,'Entrega'!$E$6:$E$9,"Ambos")+COUNTIFS('Defensa'!$B$6:$B$10,$A9,'Defensa'!$E$6:$E$10,"Diego")+COUNTIFS('Defensa'!$B$6:$B$10,$A9,'Defensa'!$E$6:$E$10,"Ambos")</f>
         <v/>
       </c>
     </row>
@@ -8825,19 +8846,19 @@
         <v/>
       </c>
       <c r="D10" s="21">
-        <f>SUMIFS('S1'!$I$6:$I$32,'S1'!$B$6:$B$32,$A10,'S1'!$E$6:$E$32,"Víctor")+SUMIFS('S1'!$I$6:$I$32,'S1'!$B$6:$B$32,$A10,'S1'!$E$6:$E$32,"Ambos")+SUMIFS('S2'!$I$6:$I$23,'S2'!$B$6:$B$23,$A10,'S2'!$E$6:$E$23,"Víctor")+SUMIFS('S2'!$I$6:$I$23,'S2'!$B$6:$B$23,$A10,'S2'!$E$6:$E$23,"Ambos")+SUMIFS('S3'!$I$6:$I$19,'S3'!$B$6:$B$19,$A10,'S3'!$E$6:$E$19,"Víctor")+SUMIFS('S3'!$I$6:$I$19,'S3'!$B$6:$B$19,$A10,'S3'!$E$6:$E$19,"Ambos")+SUMIFS('S4'!$I$6:$I$20,'S4'!$B$6:$B$20,$A10,'S4'!$E$6:$E$20,"Víctor")+SUMIFS('S4'!$I$6:$I$20,'S4'!$B$6:$B$20,$A10,'S4'!$E$6:$E$20,"Ambos")+SUMIFS('S5'!$I$6:$I$20,'S5'!$B$6:$B$20,$A10,'S5'!$E$6:$E$20,"Víctor")+SUMIFS('S5'!$I$6:$I$20,'S5'!$B$6:$B$20,$A10,'S5'!$E$6:$E$20,"Ambos")+SUMIFS('S6'!$I$6:$I$17,'S6'!$B$6:$B$17,$A10,'S6'!$E$6:$E$17,"Víctor")+SUMIFS('S6'!$I$6:$I$17,'S6'!$B$6:$B$17,$A10,'S6'!$E$6:$E$17,"Ambos")+SUMIFS('S7'!$I$6:$I$19,'S7'!$B$6:$B$19,$A10,'S7'!$E$6:$E$19,"Víctor")+SUMIFS('S7'!$I$6:$I$19,'S7'!$B$6:$B$19,$A10,'S7'!$E$6:$E$19,"Ambos")+SUMIFS('S8'!$I$6:$I$23,'S8'!$B$6:$B$23,$A10,'S8'!$E$6:$E$23,"Víctor")+SUMIFS('S8'!$I$6:$I$23,'S8'!$B$6:$B$23,$A10,'S8'!$E$6:$E$23,"Ambos")+SUMIFS('S9'!$I$6:$I$15,'S9'!$B$6:$B$15,$A10,'S9'!$E$6:$E$15,"Víctor")+SUMIFS('S9'!$I$6:$I$15,'S9'!$B$6:$B$15,$A10,'S9'!$E$6:$E$15,"Ambos")+SUMIFS('S10'!$I$6:$I$13,'S10'!$B$6:$B$13,$A10,'S10'!$E$6:$E$13,"Víctor")+SUMIFS('S10'!$I$6:$I$13,'S10'!$B$6:$B$13,$A10,'S10'!$E$6:$E$13,"Ambos")+SUMIFS('Holgura'!$I$6:$I$11,'Holgura'!$B$6:$B$11,$A10,'Holgura'!$E$6:$E$11,"Víctor")+SUMIFS('Holgura'!$I$6:$I$11,'Holgura'!$B$6:$B$11,$A10,'Holgura'!$E$6:$E$11,"Ambos")+SUMIFS('Entrega'!$I$6:$I$9,'Entrega'!$B$6:$B$9,$A10,'Entrega'!$E$6:$E$9,"Víctor")+SUMIFS('Entrega'!$I$6:$I$9,'Entrega'!$B$6:$B$9,$A10,'Entrega'!$E$6:$E$9,"Ambos")+SUMIFS('Defensa'!$I$6:$I$10,'Defensa'!$B$6:$B$10,$A10,'Defensa'!$E$6:$E$10,"Víctor")+SUMIFS('Defensa'!$I$6:$I$10,'Defensa'!$B$6:$B$10,$A10,'Defensa'!$E$6:$E$10,"Ambos")</f>
+        <f>SUMIFS('S1'!$I$6:$I$32,'S1'!$B$6:$B$32,$A10,'S1'!$E$6:$E$32,"Víctor")+SUMIFS('S1'!$I$6:$I$32,'S1'!$B$6:$B$32,$A10,'S1'!$E$6:$E$32,"Ambos")+SUMIFS('S2'!$I$6:$I$23,'S2'!$B$6:$B$23,$A10,'S2'!$E$6:$E$23,"Víctor")+SUMIFS('S2'!$I$6:$I$23,'S2'!$B$6:$B$23,$A10,'S2'!$E$6:$E$23,"Ambos")+SUMIFS('S3'!$I$6:$I$24,'S3'!$B$6:$B$24,$A10,'S3'!$E$6:$E$24,"Víctor")+SUMIFS('S3'!$I$6:$I$24,'S3'!$B$6:$B$24,$A10,'S3'!$E$6:$E$24,"Ambos")+SUMIFS('S4'!$I$6:$I$22,'S4'!$B$6:$B$22,$A10,'S4'!$E$6:$E$22,"Víctor")+SUMIFS('S4'!$I$6:$I$22,'S4'!$B$6:$B$22,$A10,'S4'!$E$6:$E$22,"Ambos")+SUMIFS('S5'!$I$6:$I$20,'S5'!$B$6:$B$20,$A10,'S5'!$E$6:$E$20,"Víctor")+SUMIFS('S5'!$I$6:$I$20,'S5'!$B$6:$B$20,$A10,'S5'!$E$6:$E$20,"Ambos")+SUMIFS('S6'!$I$6:$I$17,'S6'!$B$6:$B$17,$A10,'S6'!$E$6:$E$17,"Víctor")+SUMIFS('S6'!$I$6:$I$17,'S6'!$B$6:$B$17,$A10,'S6'!$E$6:$E$17,"Ambos")+SUMIFS('S7'!$I$6:$I$19,'S7'!$B$6:$B$19,$A10,'S7'!$E$6:$E$19,"Víctor")+SUMIFS('S7'!$I$6:$I$19,'S7'!$B$6:$B$19,$A10,'S7'!$E$6:$E$19,"Ambos")+SUMIFS('S8'!$I$6:$I$23,'S8'!$B$6:$B$23,$A10,'S8'!$E$6:$E$23,"Víctor")+SUMIFS('S8'!$I$6:$I$23,'S8'!$B$6:$B$23,$A10,'S8'!$E$6:$E$23,"Ambos")+SUMIFS('S9'!$I$6:$I$15,'S9'!$B$6:$B$15,$A10,'S9'!$E$6:$E$15,"Víctor")+SUMIFS('S9'!$I$6:$I$15,'S9'!$B$6:$B$15,$A10,'S9'!$E$6:$E$15,"Ambos")+SUMIFS('S10'!$I$6:$I$13,'S10'!$B$6:$B$13,$A10,'S10'!$E$6:$E$13,"Víctor")+SUMIFS('S10'!$I$6:$I$13,'S10'!$B$6:$B$13,$A10,'S10'!$E$6:$E$13,"Ambos")+SUMIFS('Holgura'!$I$6:$I$11,'Holgura'!$B$6:$B$11,$A10,'Holgura'!$E$6:$E$11,"Víctor")+SUMIFS('Holgura'!$I$6:$I$11,'Holgura'!$B$6:$B$11,$A10,'Holgura'!$E$6:$E$11,"Ambos")+SUMIFS('Entrega'!$I$6:$I$9,'Entrega'!$B$6:$B$9,$A10,'Entrega'!$E$6:$E$9,"Víctor")+SUMIFS('Entrega'!$I$6:$I$9,'Entrega'!$B$6:$B$9,$A10,'Entrega'!$E$6:$E$9,"Ambos")+SUMIFS('Defensa'!$I$6:$I$10,'Defensa'!$B$6:$B$10,$A10,'Defensa'!$E$6:$E$10,"Víctor")+SUMIFS('Defensa'!$I$6:$I$10,'Defensa'!$B$6:$B$10,$A10,'Defensa'!$E$6:$E$10,"Ambos")</f>
         <v/>
       </c>
       <c r="E10" s="21">
-        <f>SUMIFS('S1'!$I$6:$I$32,'S1'!$B$6:$B$32,$A10,'S1'!$E$6:$E$32,"Diego")+SUMIFS('S1'!$I$6:$I$32,'S1'!$B$6:$B$32,$A10,'S1'!$E$6:$E$32,"Ambos")+SUMIFS('S2'!$I$6:$I$23,'S2'!$B$6:$B$23,$A10,'S2'!$E$6:$E$23,"Diego")+SUMIFS('S2'!$I$6:$I$23,'S2'!$B$6:$B$23,$A10,'S2'!$E$6:$E$23,"Ambos")+SUMIFS('S3'!$I$6:$I$19,'S3'!$B$6:$B$19,$A10,'S3'!$E$6:$E$19,"Diego")+SUMIFS('S3'!$I$6:$I$19,'S3'!$B$6:$B$19,$A10,'S3'!$E$6:$E$19,"Ambos")+SUMIFS('S4'!$I$6:$I$20,'S4'!$B$6:$B$20,$A10,'S4'!$E$6:$E$20,"Diego")+SUMIFS('S4'!$I$6:$I$20,'S4'!$B$6:$B$20,$A10,'S4'!$E$6:$E$20,"Ambos")+SUMIFS('S5'!$I$6:$I$20,'S5'!$B$6:$B$20,$A10,'S5'!$E$6:$E$20,"Diego")+SUMIFS('S5'!$I$6:$I$20,'S5'!$B$6:$B$20,$A10,'S5'!$E$6:$E$20,"Ambos")+SUMIFS('S6'!$I$6:$I$17,'S6'!$B$6:$B$17,$A10,'S6'!$E$6:$E$17,"Diego")+SUMIFS('S6'!$I$6:$I$17,'S6'!$B$6:$B$17,$A10,'S6'!$E$6:$E$17,"Ambos")+SUMIFS('S7'!$I$6:$I$19,'S7'!$B$6:$B$19,$A10,'S7'!$E$6:$E$19,"Diego")+SUMIFS('S7'!$I$6:$I$19,'S7'!$B$6:$B$19,$A10,'S7'!$E$6:$E$19,"Ambos")+SUMIFS('S8'!$I$6:$I$23,'S8'!$B$6:$B$23,$A10,'S8'!$E$6:$E$23,"Diego")+SUMIFS('S8'!$I$6:$I$23,'S8'!$B$6:$B$23,$A10,'S8'!$E$6:$E$23,"Ambos")+SUMIFS('S9'!$I$6:$I$15,'S9'!$B$6:$B$15,$A10,'S9'!$E$6:$E$15,"Diego")+SUMIFS('S9'!$I$6:$I$15,'S9'!$B$6:$B$15,$A10,'S9'!$E$6:$E$15,"Ambos")+SUMIFS('S10'!$I$6:$I$13,'S10'!$B$6:$B$13,$A10,'S10'!$E$6:$E$13,"Diego")+SUMIFS('S10'!$I$6:$I$13,'S10'!$B$6:$B$13,$A10,'S10'!$E$6:$E$13,"Ambos")+SUMIFS('Holgura'!$I$6:$I$11,'Holgura'!$B$6:$B$11,$A10,'Holgura'!$E$6:$E$11,"Diego")+SUMIFS('Holgura'!$I$6:$I$11,'Holgura'!$B$6:$B$11,$A10,'Holgura'!$E$6:$E$11,"Ambos")+SUMIFS('Entrega'!$I$6:$I$9,'Entrega'!$B$6:$B$9,$A10,'Entrega'!$E$6:$E$9,"Diego")+SUMIFS('Entrega'!$I$6:$I$9,'Entrega'!$B$6:$B$9,$A10,'Entrega'!$E$6:$E$9,"Ambos")+SUMIFS('Defensa'!$I$6:$I$10,'Defensa'!$B$6:$B$10,$A10,'Defensa'!$E$6:$E$10,"Diego")+SUMIFS('Defensa'!$I$6:$I$10,'Defensa'!$B$6:$B$10,$A10,'Defensa'!$E$6:$E$10,"Ambos")</f>
+        <f>SUMIFS('S1'!$I$6:$I$32,'S1'!$B$6:$B$32,$A10,'S1'!$E$6:$E$32,"Diego")+SUMIFS('S1'!$I$6:$I$32,'S1'!$B$6:$B$32,$A10,'S1'!$E$6:$E$32,"Ambos")+SUMIFS('S2'!$I$6:$I$23,'S2'!$B$6:$B$23,$A10,'S2'!$E$6:$E$23,"Diego")+SUMIFS('S2'!$I$6:$I$23,'S2'!$B$6:$B$23,$A10,'S2'!$E$6:$E$23,"Ambos")+SUMIFS('S3'!$I$6:$I$24,'S3'!$B$6:$B$24,$A10,'S3'!$E$6:$E$24,"Diego")+SUMIFS('S3'!$I$6:$I$24,'S3'!$B$6:$B$24,$A10,'S3'!$E$6:$E$24,"Ambos")+SUMIFS('S4'!$I$6:$I$22,'S4'!$B$6:$B$22,$A10,'S4'!$E$6:$E$22,"Diego")+SUMIFS('S4'!$I$6:$I$22,'S4'!$B$6:$B$22,$A10,'S4'!$E$6:$E$22,"Ambos")+SUMIFS('S5'!$I$6:$I$20,'S5'!$B$6:$B$20,$A10,'S5'!$E$6:$E$20,"Diego")+SUMIFS('S5'!$I$6:$I$20,'S5'!$B$6:$B$20,$A10,'S5'!$E$6:$E$20,"Ambos")+SUMIFS('S6'!$I$6:$I$17,'S6'!$B$6:$B$17,$A10,'S6'!$E$6:$E$17,"Diego")+SUMIFS('S6'!$I$6:$I$17,'S6'!$B$6:$B$17,$A10,'S6'!$E$6:$E$17,"Ambos")+SUMIFS('S7'!$I$6:$I$19,'S7'!$B$6:$B$19,$A10,'S7'!$E$6:$E$19,"Diego")+SUMIFS('S7'!$I$6:$I$19,'S7'!$B$6:$B$19,$A10,'S7'!$E$6:$E$19,"Ambos")+SUMIFS('S8'!$I$6:$I$23,'S8'!$B$6:$B$23,$A10,'S8'!$E$6:$E$23,"Diego")+SUMIFS('S8'!$I$6:$I$23,'S8'!$B$6:$B$23,$A10,'S8'!$E$6:$E$23,"Ambos")+SUMIFS('S9'!$I$6:$I$15,'S9'!$B$6:$B$15,$A10,'S9'!$E$6:$E$15,"Diego")+SUMIFS('S9'!$I$6:$I$15,'S9'!$B$6:$B$15,$A10,'S9'!$E$6:$E$15,"Ambos")+SUMIFS('S10'!$I$6:$I$13,'S10'!$B$6:$B$13,$A10,'S10'!$E$6:$E$13,"Diego")+SUMIFS('S10'!$I$6:$I$13,'S10'!$B$6:$B$13,$A10,'S10'!$E$6:$E$13,"Ambos")+SUMIFS('Holgura'!$I$6:$I$11,'Holgura'!$B$6:$B$11,$A10,'Holgura'!$E$6:$E$11,"Diego")+SUMIFS('Holgura'!$I$6:$I$11,'Holgura'!$B$6:$B$11,$A10,'Holgura'!$E$6:$E$11,"Ambos")+SUMIFS('Entrega'!$I$6:$I$9,'Entrega'!$B$6:$B$9,$A10,'Entrega'!$E$6:$E$9,"Diego")+SUMIFS('Entrega'!$I$6:$I$9,'Entrega'!$B$6:$B$9,$A10,'Entrega'!$E$6:$E$9,"Ambos")+SUMIFS('Defensa'!$I$6:$I$10,'Defensa'!$B$6:$B$10,$A10,'Defensa'!$E$6:$E$10,"Diego")+SUMIFS('Defensa'!$I$6:$I$10,'Defensa'!$B$6:$B$10,$A10,'Defensa'!$E$6:$E$10,"Ambos")</f>
         <v/>
       </c>
       <c r="F10" s="21">
-        <f>COUNTIFS('S1'!$B$6:$B$32,$A10,'S1'!$E$6:$E$32,"Víctor")+COUNTIFS('S1'!$B$6:$B$32,$A10,'S1'!$E$6:$E$32,"Ambos")+COUNTIFS('S2'!$B$6:$B$23,$A10,'S2'!$E$6:$E$23,"Víctor")+COUNTIFS('S2'!$B$6:$B$23,$A10,'S2'!$E$6:$E$23,"Ambos")+COUNTIFS('S3'!$B$6:$B$19,$A10,'S3'!$E$6:$E$19,"Víctor")+COUNTIFS('S3'!$B$6:$B$19,$A10,'S3'!$E$6:$E$19,"Ambos")+COUNTIFS('S4'!$B$6:$B$20,$A10,'S4'!$E$6:$E$20,"Víctor")+COUNTIFS('S4'!$B$6:$B$20,$A10,'S4'!$E$6:$E$20,"Ambos")+COUNTIFS('S5'!$B$6:$B$20,$A10,'S5'!$E$6:$E$20,"Víctor")+COUNTIFS('S5'!$B$6:$B$20,$A10,'S5'!$E$6:$E$20,"Ambos")+COUNTIFS('S6'!$B$6:$B$17,$A10,'S6'!$E$6:$E$17,"Víctor")+COUNTIFS('S6'!$B$6:$B$17,$A10,'S6'!$E$6:$E$17,"Ambos")+COUNTIFS('S7'!$B$6:$B$19,$A10,'S7'!$E$6:$E$19,"Víctor")+COUNTIFS('S7'!$B$6:$B$19,$A10,'S7'!$E$6:$E$19,"Ambos")+COUNTIFS('S8'!$B$6:$B$23,$A10,'S8'!$E$6:$E$23,"Víctor")+COUNTIFS('S8'!$B$6:$B$23,$A10,'S8'!$E$6:$E$23,"Ambos")+COUNTIFS('S9'!$B$6:$B$15,$A10,'S9'!$E$6:$E$15,"Víctor")+COUNTIFS('S9'!$B$6:$B$15,$A10,'S9'!$E$6:$E$15,"Ambos")+COUNTIFS('S10'!$B$6:$B$13,$A10,'S10'!$E$6:$E$13,"Víctor")+COUNTIFS('S10'!$B$6:$B$13,$A10,'S10'!$E$6:$E$13,"Ambos")+COUNTIFS('Holgura'!$B$6:$B$11,$A10,'Holgura'!$E$6:$E$11,"Víctor")+COUNTIFS('Holgura'!$B$6:$B$11,$A10,'Holgura'!$E$6:$E$11,"Ambos")+COUNTIFS('Entrega'!$B$6:$B$9,$A10,'Entrega'!$E$6:$E$9,"Víctor")+COUNTIFS('Entrega'!$B$6:$B$9,$A10,'Entrega'!$E$6:$E$9,"Ambos")+COUNTIFS('Defensa'!$B$6:$B$10,$A10,'Defensa'!$E$6:$E$10,"Víctor")+COUNTIFS('Defensa'!$B$6:$B$10,$A10,'Defensa'!$E$6:$E$10,"Ambos")</f>
+        <f>COUNTIFS('S1'!$B$6:$B$32,$A10,'S1'!$E$6:$E$32,"Víctor")+COUNTIFS('S1'!$B$6:$B$32,$A10,'S1'!$E$6:$E$32,"Ambos")+COUNTIFS('S2'!$B$6:$B$23,$A10,'S2'!$E$6:$E$23,"Víctor")+COUNTIFS('S2'!$B$6:$B$23,$A10,'S2'!$E$6:$E$23,"Ambos")+COUNTIFS('S3'!$B$6:$B$24,$A10,'S3'!$E$6:$E$24,"Víctor")+COUNTIFS('S3'!$B$6:$B$24,$A10,'S3'!$E$6:$E$24,"Ambos")+COUNTIFS('S4'!$B$6:$B$22,$A10,'S4'!$E$6:$E$22,"Víctor")+COUNTIFS('S4'!$B$6:$B$22,$A10,'S4'!$E$6:$E$22,"Ambos")+COUNTIFS('S5'!$B$6:$B$20,$A10,'S5'!$E$6:$E$20,"Víctor")+COUNTIFS('S5'!$B$6:$B$20,$A10,'S5'!$E$6:$E$20,"Ambos")+COUNTIFS('S6'!$B$6:$B$17,$A10,'S6'!$E$6:$E$17,"Víctor")+COUNTIFS('S6'!$B$6:$B$17,$A10,'S6'!$E$6:$E$17,"Ambos")+COUNTIFS('S7'!$B$6:$B$19,$A10,'S7'!$E$6:$E$19,"Víctor")+COUNTIFS('S7'!$B$6:$B$19,$A10,'S7'!$E$6:$E$19,"Ambos")+COUNTIFS('S8'!$B$6:$B$23,$A10,'S8'!$E$6:$E$23,"Víctor")+COUNTIFS('S8'!$B$6:$B$23,$A10,'S8'!$E$6:$E$23,"Ambos")+COUNTIFS('S9'!$B$6:$B$15,$A10,'S9'!$E$6:$E$15,"Víctor")+COUNTIFS('S9'!$B$6:$B$15,$A10,'S9'!$E$6:$E$15,"Ambos")+COUNTIFS('S10'!$B$6:$B$13,$A10,'S10'!$E$6:$E$13,"Víctor")+COUNTIFS('S10'!$B$6:$B$13,$A10,'S10'!$E$6:$E$13,"Ambos")+COUNTIFS('Holgura'!$B$6:$B$11,$A10,'Holgura'!$E$6:$E$11,"Víctor")+COUNTIFS('Holgura'!$B$6:$B$11,$A10,'Holgura'!$E$6:$E$11,"Ambos")+COUNTIFS('Entrega'!$B$6:$B$9,$A10,'Entrega'!$E$6:$E$9,"Víctor")+COUNTIFS('Entrega'!$B$6:$B$9,$A10,'Entrega'!$E$6:$E$9,"Ambos")+COUNTIFS('Defensa'!$B$6:$B$10,$A10,'Defensa'!$E$6:$E$10,"Víctor")+COUNTIFS('Defensa'!$B$6:$B$10,$A10,'Defensa'!$E$6:$E$10,"Ambos")</f>
         <v/>
       </c>
       <c r="G10" s="21">
-        <f>COUNTIFS('S1'!$B$6:$B$32,$A10,'S1'!$E$6:$E$32,"Diego")+COUNTIFS('S1'!$B$6:$B$32,$A10,'S1'!$E$6:$E$32,"Ambos")+COUNTIFS('S2'!$B$6:$B$23,$A10,'S2'!$E$6:$E$23,"Diego")+COUNTIFS('S2'!$B$6:$B$23,$A10,'S2'!$E$6:$E$23,"Ambos")+COUNTIFS('S3'!$B$6:$B$19,$A10,'S3'!$E$6:$E$19,"Diego")+COUNTIFS('S3'!$B$6:$B$19,$A10,'S3'!$E$6:$E$19,"Ambos")+COUNTIFS('S4'!$B$6:$B$20,$A10,'S4'!$E$6:$E$20,"Diego")+COUNTIFS('S4'!$B$6:$B$20,$A10,'S4'!$E$6:$E$20,"Ambos")+COUNTIFS('S5'!$B$6:$B$20,$A10,'S5'!$E$6:$E$20,"Diego")+COUNTIFS('S5'!$B$6:$B$20,$A10,'S5'!$E$6:$E$20,"Ambos")+COUNTIFS('S6'!$B$6:$B$17,$A10,'S6'!$E$6:$E$17,"Diego")+COUNTIFS('S6'!$B$6:$B$17,$A10,'S6'!$E$6:$E$17,"Ambos")+COUNTIFS('S7'!$B$6:$B$19,$A10,'S7'!$E$6:$E$19,"Diego")+COUNTIFS('S7'!$B$6:$B$19,$A10,'S7'!$E$6:$E$19,"Ambos")+COUNTIFS('S8'!$B$6:$B$23,$A10,'S8'!$E$6:$E$23,"Diego")+COUNTIFS('S8'!$B$6:$B$23,$A10,'S8'!$E$6:$E$23,"Ambos")+COUNTIFS('S9'!$B$6:$B$15,$A10,'S9'!$E$6:$E$15,"Diego")+COUNTIFS('S9'!$B$6:$B$15,$A10,'S9'!$E$6:$E$15,"Ambos")+COUNTIFS('S10'!$B$6:$B$13,$A10,'S10'!$E$6:$E$13,"Diego")+COUNTIFS('S10'!$B$6:$B$13,$A10,'S10'!$E$6:$E$13,"Ambos")+COUNTIFS('Holgura'!$B$6:$B$11,$A10,'Holgura'!$E$6:$E$11,"Diego")+COUNTIFS('Holgura'!$B$6:$B$11,$A10,'Holgura'!$E$6:$E$11,"Ambos")+COUNTIFS('Entrega'!$B$6:$B$9,$A10,'Entrega'!$E$6:$E$9,"Diego")+COUNTIFS('Entrega'!$B$6:$B$9,$A10,'Entrega'!$E$6:$E$9,"Ambos")+COUNTIFS('Defensa'!$B$6:$B$10,$A10,'Defensa'!$E$6:$E$10,"Diego")+COUNTIFS('Defensa'!$B$6:$B$10,$A10,'Defensa'!$E$6:$E$10,"Ambos")</f>
+        <f>COUNTIFS('S1'!$B$6:$B$32,$A10,'S1'!$E$6:$E$32,"Diego")+COUNTIFS('S1'!$B$6:$B$32,$A10,'S1'!$E$6:$E$32,"Ambos")+COUNTIFS('S2'!$B$6:$B$23,$A10,'S2'!$E$6:$E$23,"Diego")+COUNTIFS('S2'!$B$6:$B$23,$A10,'S2'!$E$6:$E$23,"Ambos")+COUNTIFS('S3'!$B$6:$B$24,$A10,'S3'!$E$6:$E$24,"Diego")+COUNTIFS('S3'!$B$6:$B$24,$A10,'S3'!$E$6:$E$24,"Ambos")+COUNTIFS('S4'!$B$6:$B$22,$A10,'S4'!$E$6:$E$22,"Diego")+COUNTIFS('S4'!$B$6:$B$22,$A10,'S4'!$E$6:$E$22,"Ambos")+COUNTIFS('S5'!$B$6:$B$20,$A10,'S5'!$E$6:$E$20,"Diego")+COUNTIFS('S5'!$B$6:$B$20,$A10,'S5'!$E$6:$E$20,"Ambos")+COUNTIFS('S6'!$B$6:$B$17,$A10,'S6'!$E$6:$E$17,"Diego")+COUNTIFS('S6'!$B$6:$B$17,$A10,'S6'!$E$6:$E$17,"Ambos")+COUNTIFS('S7'!$B$6:$B$19,$A10,'S7'!$E$6:$E$19,"Diego")+COUNTIFS('S7'!$B$6:$B$19,$A10,'S7'!$E$6:$E$19,"Ambos")+COUNTIFS('S8'!$B$6:$B$23,$A10,'S8'!$E$6:$E$23,"Diego")+COUNTIFS('S8'!$B$6:$B$23,$A10,'S8'!$E$6:$E$23,"Ambos")+COUNTIFS('S9'!$B$6:$B$15,$A10,'S9'!$E$6:$E$15,"Diego")+COUNTIFS('S9'!$B$6:$B$15,$A10,'S9'!$E$6:$E$15,"Ambos")+COUNTIFS('S10'!$B$6:$B$13,$A10,'S10'!$E$6:$E$13,"Diego")+COUNTIFS('S10'!$B$6:$B$13,$A10,'S10'!$E$6:$E$13,"Ambos")+COUNTIFS('Holgura'!$B$6:$B$11,$A10,'Holgura'!$E$6:$E$11,"Diego")+COUNTIFS('Holgura'!$B$6:$B$11,$A10,'Holgura'!$E$6:$E$11,"Ambos")+COUNTIFS('Entrega'!$B$6:$B$9,$A10,'Entrega'!$E$6:$E$9,"Diego")+COUNTIFS('Entrega'!$B$6:$B$9,$A10,'Entrega'!$E$6:$E$9,"Ambos")+COUNTIFS('Defensa'!$B$6:$B$10,$A10,'Defensa'!$E$6:$E$10,"Diego")+COUNTIFS('Defensa'!$B$6:$B$10,$A10,'Defensa'!$E$6:$E$10,"Ambos")</f>
         <v/>
       </c>
     </row>
@@ -8854,19 +8875,19 @@
         <v/>
       </c>
       <c r="D11" s="21">
-        <f>SUMIFS('S1'!$I$6:$I$32,'S1'!$B$6:$B$32,$A11,'S1'!$E$6:$E$32,"Víctor")+SUMIFS('S1'!$I$6:$I$32,'S1'!$B$6:$B$32,$A11,'S1'!$E$6:$E$32,"Ambos")+SUMIFS('S2'!$I$6:$I$23,'S2'!$B$6:$B$23,$A11,'S2'!$E$6:$E$23,"Víctor")+SUMIFS('S2'!$I$6:$I$23,'S2'!$B$6:$B$23,$A11,'S2'!$E$6:$E$23,"Ambos")+SUMIFS('S3'!$I$6:$I$19,'S3'!$B$6:$B$19,$A11,'S3'!$E$6:$E$19,"Víctor")+SUMIFS('S3'!$I$6:$I$19,'S3'!$B$6:$B$19,$A11,'S3'!$E$6:$E$19,"Ambos")+SUMIFS('S4'!$I$6:$I$20,'S4'!$B$6:$B$20,$A11,'S4'!$E$6:$E$20,"Víctor")+SUMIFS('S4'!$I$6:$I$20,'S4'!$B$6:$B$20,$A11,'S4'!$E$6:$E$20,"Ambos")+SUMIFS('S5'!$I$6:$I$20,'S5'!$B$6:$B$20,$A11,'S5'!$E$6:$E$20,"Víctor")+SUMIFS('S5'!$I$6:$I$20,'S5'!$B$6:$B$20,$A11,'S5'!$E$6:$E$20,"Ambos")+SUMIFS('S6'!$I$6:$I$17,'S6'!$B$6:$B$17,$A11,'S6'!$E$6:$E$17,"Víctor")+SUMIFS('S6'!$I$6:$I$17,'S6'!$B$6:$B$17,$A11,'S6'!$E$6:$E$17,"Ambos")+SUMIFS('S7'!$I$6:$I$19,'S7'!$B$6:$B$19,$A11,'S7'!$E$6:$E$19,"Víctor")+SUMIFS('S7'!$I$6:$I$19,'S7'!$B$6:$B$19,$A11,'S7'!$E$6:$E$19,"Ambos")+SUMIFS('S8'!$I$6:$I$23,'S8'!$B$6:$B$23,$A11,'S8'!$E$6:$E$23,"Víctor")+SUMIFS('S8'!$I$6:$I$23,'S8'!$B$6:$B$23,$A11,'S8'!$E$6:$E$23,"Ambos")+SUMIFS('S9'!$I$6:$I$15,'S9'!$B$6:$B$15,$A11,'S9'!$E$6:$E$15,"Víctor")+SUMIFS('S9'!$I$6:$I$15,'S9'!$B$6:$B$15,$A11,'S9'!$E$6:$E$15,"Ambos")+SUMIFS('S10'!$I$6:$I$13,'S10'!$B$6:$B$13,$A11,'S10'!$E$6:$E$13,"Víctor")+SUMIFS('S10'!$I$6:$I$13,'S10'!$B$6:$B$13,$A11,'S10'!$E$6:$E$13,"Ambos")+SUMIFS('Holgura'!$I$6:$I$11,'Holgura'!$B$6:$B$11,$A11,'Holgura'!$E$6:$E$11,"Víctor")+SUMIFS('Holgura'!$I$6:$I$11,'Holgura'!$B$6:$B$11,$A11,'Holgura'!$E$6:$E$11,"Ambos")+SUMIFS('Entrega'!$I$6:$I$9,'Entrega'!$B$6:$B$9,$A11,'Entrega'!$E$6:$E$9,"Víctor")+SUMIFS('Entrega'!$I$6:$I$9,'Entrega'!$B$6:$B$9,$A11,'Entrega'!$E$6:$E$9,"Ambos")+SUMIFS('Defensa'!$I$6:$I$10,'Defensa'!$B$6:$B$10,$A11,'Defensa'!$E$6:$E$10,"Víctor")+SUMIFS('Defensa'!$I$6:$I$10,'Defensa'!$B$6:$B$10,$A11,'Defensa'!$E$6:$E$10,"Ambos")</f>
+        <f>SUMIFS('S1'!$I$6:$I$32,'S1'!$B$6:$B$32,$A11,'S1'!$E$6:$E$32,"Víctor")+SUMIFS('S1'!$I$6:$I$32,'S1'!$B$6:$B$32,$A11,'S1'!$E$6:$E$32,"Ambos")+SUMIFS('S2'!$I$6:$I$23,'S2'!$B$6:$B$23,$A11,'S2'!$E$6:$E$23,"Víctor")+SUMIFS('S2'!$I$6:$I$23,'S2'!$B$6:$B$23,$A11,'S2'!$E$6:$E$23,"Ambos")+SUMIFS('S3'!$I$6:$I$24,'S3'!$B$6:$B$24,$A11,'S3'!$E$6:$E$24,"Víctor")+SUMIFS('S3'!$I$6:$I$24,'S3'!$B$6:$B$24,$A11,'S3'!$E$6:$E$24,"Ambos")+SUMIFS('S4'!$I$6:$I$22,'S4'!$B$6:$B$22,$A11,'S4'!$E$6:$E$22,"Víctor")+SUMIFS('S4'!$I$6:$I$22,'S4'!$B$6:$B$22,$A11,'S4'!$E$6:$E$22,"Ambos")+SUMIFS('S5'!$I$6:$I$20,'S5'!$B$6:$B$20,$A11,'S5'!$E$6:$E$20,"Víctor")+SUMIFS('S5'!$I$6:$I$20,'S5'!$B$6:$B$20,$A11,'S5'!$E$6:$E$20,"Ambos")+SUMIFS('S6'!$I$6:$I$17,'S6'!$B$6:$B$17,$A11,'S6'!$E$6:$E$17,"Víctor")+SUMIFS('S6'!$I$6:$I$17,'S6'!$B$6:$B$17,$A11,'S6'!$E$6:$E$17,"Ambos")+SUMIFS('S7'!$I$6:$I$19,'S7'!$B$6:$B$19,$A11,'S7'!$E$6:$E$19,"Víctor")+SUMIFS('S7'!$I$6:$I$19,'S7'!$B$6:$B$19,$A11,'S7'!$E$6:$E$19,"Ambos")+SUMIFS('S8'!$I$6:$I$23,'S8'!$B$6:$B$23,$A11,'S8'!$E$6:$E$23,"Víctor")+SUMIFS('S8'!$I$6:$I$23,'S8'!$B$6:$B$23,$A11,'S8'!$E$6:$E$23,"Ambos")+SUMIFS('S9'!$I$6:$I$15,'S9'!$B$6:$B$15,$A11,'S9'!$E$6:$E$15,"Víctor")+SUMIFS('S9'!$I$6:$I$15,'S9'!$B$6:$B$15,$A11,'S9'!$E$6:$E$15,"Ambos")+SUMIFS('S10'!$I$6:$I$13,'S10'!$B$6:$B$13,$A11,'S10'!$E$6:$E$13,"Víctor")+SUMIFS('S10'!$I$6:$I$13,'S10'!$B$6:$B$13,$A11,'S10'!$E$6:$E$13,"Ambos")+SUMIFS('Holgura'!$I$6:$I$11,'Holgura'!$B$6:$B$11,$A11,'Holgura'!$E$6:$E$11,"Víctor")+SUMIFS('Holgura'!$I$6:$I$11,'Holgura'!$B$6:$B$11,$A11,'Holgura'!$E$6:$E$11,"Ambos")+SUMIFS('Entrega'!$I$6:$I$9,'Entrega'!$B$6:$B$9,$A11,'Entrega'!$E$6:$E$9,"Víctor")+SUMIFS('Entrega'!$I$6:$I$9,'Entrega'!$B$6:$B$9,$A11,'Entrega'!$E$6:$E$9,"Ambos")+SUMIFS('Defensa'!$I$6:$I$10,'Defensa'!$B$6:$B$10,$A11,'Defensa'!$E$6:$E$10,"Víctor")+SUMIFS('Defensa'!$I$6:$I$10,'Defensa'!$B$6:$B$10,$A11,'Defensa'!$E$6:$E$10,"Ambos")</f>
         <v/>
       </c>
       <c r="E11" s="21">
-        <f>SUMIFS('S1'!$I$6:$I$32,'S1'!$B$6:$B$32,$A11,'S1'!$E$6:$E$32,"Diego")+SUMIFS('S1'!$I$6:$I$32,'S1'!$B$6:$B$32,$A11,'S1'!$E$6:$E$32,"Ambos")+SUMIFS('S2'!$I$6:$I$23,'S2'!$B$6:$B$23,$A11,'S2'!$E$6:$E$23,"Diego")+SUMIFS('S2'!$I$6:$I$23,'S2'!$B$6:$B$23,$A11,'S2'!$E$6:$E$23,"Ambos")+SUMIFS('S3'!$I$6:$I$19,'S3'!$B$6:$B$19,$A11,'S3'!$E$6:$E$19,"Diego")+SUMIFS('S3'!$I$6:$I$19,'S3'!$B$6:$B$19,$A11,'S3'!$E$6:$E$19,"Ambos")+SUMIFS('S4'!$I$6:$I$20,'S4'!$B$6:$B$20,$A11,'S4'!$E$6:$E$20,"Diego")+SUMIFS('S4'!$I$6:$I$20,'S4'!$B$6:$B$20,$A11,'S4'!$E$6:$E$20,"Ambos")+SUMIFS('S5'!$I$6:$I$20,'S5'!$B$6:$B$20,$A11,'S5'!$E$6:$E$20,"Diego")+SUMIFS('S5'!$I$6:$I$20,'S5'!$B$6:$B$20,$A11,'S5'!$E$6:$E$20,"Ambos")+SUMIFS('S6'!$I$6:$I$17,'S6'!$B$6:$B$17,$A11,'S6'!$E$6:$E$17,"Diego")+SUMIFS('S6'!$I$6:$I$17,'S6'!$B$6:$B$17,$A11,'S6'!$E$6:$E$17,"Ambos")+SUMIFS('S7'!$I$6:$I$19,'S7'!$B$6:$B$19,$A11,'S7'!$E$6:$E$19,"Diego")+SUMIFS('S7'!$I$6:$I$19,'S7'!$B$6:$B$19,$A11,'S7'!$E$6:$E$19,"Ambos")+SUMIFS('S8'!$I$6:$I$23,'S8'!$B$6:$B$23,$A11,'S8'!$E$6:$E$23,"Diego")+SUMIFS('S8'!$I$6:$I$23,'S8'!$B$6:$B$23,$A11,'S8'!$E$6:$E$23,"Ambos")+SUMIFS('S9'!$I$6:$I$15,'S9'!$B$6:$B$15,$A11,'S9'!$E$6:$E$15,"Diego")+SUMIFS('S9'!$I$6:$I$15,'S9'!$B$6:$B$15,$A11,'S9'!$E$6:$E$15,"Ambos")+SUMIFS('S10'!$I$6:$I$13,'S10'!$B$6:$B$13,$A11,'S10'!$E$6:$E$13,"Diego")+SUMIFS('S10'!$I$6:$I$13,'S10'!$B$6:$B$13,$A11,'S10'!$E$6:$E$13,"Ambos")+SUMIFS('Holgura'!$I$6:$I$11,'Holgura'!$B$6:$B$11,$A11,'Holgura'!$E$6:$E$11,"Diego")+SUMIFS('Holgura'!$I$6:$I$11,'Holgura'!$B$6:$B$11,$A11,'Holgura'!$E$6:$E$11,"Ambos")+SUMIFS('Entrega'!$I$6:$I$9,'Entrega'!$B$6:$B$9,$A11,'Entrega'!$E$6:$E$9,"Diego")+SUMIFS('Entrega'!$I$6:$I$9,'Entrega'!$B$6:$B$9,$A11,'Entrega'!$E$6:$E$9,"Ambos")+SUMIFS('Defensa'!$I$6:$I$10,'Defensa'!$B$6:$B$10,$A11,'Defensa'!$E$6:$E$10,"Diego")+SUMIFS('Defensa'!$I$6:$I$10,'Defensa'!$B$6:$B$10,$A11,'Defensa'!$E$6:$E$10,"Ambos")</f>
+        <f>SUMIFS('S1'!$I$6:$I$32,'S1'!$B$6:$B$32,$A11,'S1'!$E$6:$E$32,"Diego")+SUMIFS('S1'!$I$6:$I$32,'S1'!$B$6:$B$32,$A11,'S1'!$E$6:$E$32,"Ambos")+SUMIFS('S2'!$I$6:$I$23,'S2'!$B$6:$B$23,$A11,'S2'!$E$6:$E$23,"Diego")+SUMIFS('S2'!$I$6:$I$23,'S2'!$B$6:$B$23,$A11,'S2'!$E$6:$E$23,"Ambos")+SUMIFS('S3'!$I$6:$I$24,'S3'!$B$6:$B$24,$A11,'S3'!$E$6:$E$24,"Diego")+SUMIFS('S3'!$I$6:$I$24,'S3'!$B$6:$B$24,$A11,'S3'!$E$6:$E$24,"Ambos")+SUMIFS('S4'!$I$6:$I$22,'S4'!$B$6:$B$22,$A11,'S4'!$E$6:$E$22,"Diego")+SUMIFS('S4'!$I$6:$I$22,'S4'!$B$6:$B$22,$A11,'S4'!$E$6:$E$22,"Ambos")+SUMIFS('S5'!$I$6:$I$20,'S5'!$B$6:$B$20,$A11,'S5'!$E$6:$E$20,"Diego")+SUMIFS('S5'!$I$6:$I$20,'S5'!$B$6:$B$20,$A11,'S5'!$E$6:$E$20,"Ambos")+SUMIFS('S6'!$I$6:$I$17,'S6'!$B$6:$B$17,$A11,'S6'!$E$6:$E$17,"Diego")+SUMIFS('S6'!$I$6:$I$17,'S6'!$B$6:$B$17,$A11,'S6'!$E$6:$E$17,"Ambos")+SUMIFS('S7'!$I$6:$I$19,'S7'!$B$6:$B$19,$A11,'S7'!$E$6:$E$19,"Diego")+SUMIFS('S7'!$I$6:$I$19,'S7'!$B$6:$B$19,$A11,'S7'!$E$6:$E$19,"Ambos")+SUMIFS('S8'!$I$6:$I$23,'S8'!$B$6:$B$23,$A11,'S8'!$E$6:$E$23,"Diego")+SUMIFS('S8'!$I$6:$I$23,'S8'!$B$6:$B$23,$A11,'S8'!$E$6:$E$23,"Ambos")+SUMIFS('S9'!$I$6:$I$15,'S9'!$B$6:$B$15,$A11,'S9'!$E$6:$E$15,"Diego")+SUMIFS('S9'!$I$6:$I$15,'S9'!$B$6:$B$15,$A11,'S9'!$E$6:$E$15,"Ambos")+SUMIFS('S10'!$I$6:$I$13,'S10'!$B$6:$B$13,$A11,'S10'!$E$6:$E$13,"Diego")+SUMIFS('S10'!$I$6:$I$13,'S10'!$B$6:$B$13,$A11,'S10'!$E$6:$E$13,"Ambos")+SUMIFS('Holgura'!$I$6:$I$11,'Holgura'!$B$6:$B$11,$A11,'Holgura'!$E$6:$E$11,"Diego")+SUMIFS('Holgura'!$I$6:$I$11,'Holgura'!$B$6:$B$11,$A11,'Holgura'!$E$6:$E$11,"Ambos")+SUMIFS('Entrega'!$I$6:$I$9,'Entrega'!$B$6:$B$9,$A11,'Entrega'!$E$6:$E$9,"Diego")+SUMIFS('Entrega'!$I$6:$I$9,'Entrega'!$B$6:$B$9,$A11,'Entrega'!$E$6:$E$9,"Ambos")+SUMIFS('Defensa'!$I$6:$I$10,'Defensa'!$B$6:$B$10,$A11,'Defensa'!$E$6:$E$10,"Diego")+SUMIFS('Defensa'!$I$6:$I$10,'Defensa'!$B$6:$B$10,$A11,'Defensa'!$E$6:$E$10,"Ambos")</f>
         <v/>
       </c>
       <c r="F11" s="21">
-        <f>COUNTIFS('S1'!$B$6:$B$32,$A11,'S1'!$E$6:$E$32,"Víctor")+COUNTIFS('S1'!$B$6:$B$32,$A11,'S1'!$E$6:$E$32,"Ambos")+COUNTIFS('S2'!$B$6:$B$23,$A11,'S2'!$E$6:$E$23,"Víctor")+COUNTIFS('S2'!$B$6:$B$23,$A11,'S2'!$E$6:$E$23,"Ambos")+COUNTIFS('S3'!$B$6:$B$19,$A11,'S3'!$E$6:$E$19,"Víctor")+COUNTIFS('S3'!$B$6:$B$19,$A11,'S3'!$E$6:$E$19,"Ambos")+COUNTIFS('S4'!$B$6:$B$20,$A11,'S4'!$E$6:$E$20,"Víctor")+COUNTIFS('S4'!$B$6:$B$20,$A11,'S4'!$E$6:$E$20,"Ambos")+COUNTIFS('S5'!$B$6:$B$20,$A11,'S5'!$E$6:$E$20,"Víctor")+COUNTIFS('S5'!$B$6:$B$20,$A11,'S5'!$E$6:$E$20,"Ambos")+COUNTIFS('S6'!$B$6:$B$17,$A11,'S6'!$E$6:$E$17,"Víctor")+COUNTIFS('S6'!$B$6:$B$17,$A11,'S6'!$E$6:$E$17,"Ambos")+COUNTIFS('S7'!$B$6:$B$19,$A11,'S7'!$E$6:$E$19,"Víctor")+COUNTIFS('S7'!$B$6:$B$19,$A11,'S7'!$E$6:$E$19,"Ambos")+COUNTIFS('S8'!$B$6:$B$23,$A11,'S8'!$E$6:$E$23,"Víctor")+COUNTIFS('S8'!$B$6:$B$23,$A11,'S8'!$E$6:$E$23,"Ambos")+COUNTIFS('S9'!$B$6:$B$15,$A11,'S9'!$E$6:$E$15,"Víctor")+COUNTIFS('S9'!$B$6:$B$15,$A11,'S9'!$E$6:$E$15,"Ambos")+COUNTIFS('S10'!$B$6:$B$13,$A11,'S10'!$E$6:$E$13,"Víctor")+COUNTIFS('S10'!$B$6:$B$13,$A11,'S10'!$E$6:$E$13,"Ambos")+COUNTIFS('Holgura'!$B$6:$B$11,$A11,'Holgura'!$E$6:$E$11,"Víctor")+COUNTIFS('Holgura'!$B$6:$B$11,$A11,'Holgura'!$E$6:$E$11,"Ambos")+COUNTIFS('Entrega'!$B$6:$B$9,$A11,'Entrega'!$E$6:$E$9,"Víctor")+COUNTIFS('Entrega'!$B$6:$B$9,$A11,'Entrega'!$E$6:$E$9,"Ambos")+COUNTIFS('Defensa'!$B$6:$B$10,$A11,'Defensa'!$E$6:$E$10,"Víctor")+COUNTIFS('Defensa'!$B$6:$B$10,$A11,'Defensa'!$E$6:$E$10,"Ambos")</f>
+        <f>COUNTIFS('S1'!$B$6:$B$32,$A11,'S1'!$E$6:$E$32,"Víctor")+COUNTIFS('S1'!$B$6:$B$32,$A11,'S1'!$E$6:$E$32,"Ambos")+COUNTIFS('S2'!$B$6:$B$23,$A11,'S2'!$E$6:$E$23,"Víctor")+COUNTIFS('S2'!$B$6:$B$23,$A11,'S2'!$E$6:$E$23,"Ambos")+COUNTIFS('S3'!$B$6:$B$24,$A11,'S3'!$E$6:$E$24,"Víctor")+COUNTIFS('S3'!$B$6:$B$24,$A11,'S3'!$E$6:$E$24,"Ambos")+COUNTIFS('S4'!$B$6:$B$22,$A11,'S4'!$E$6:$E$22,"Víctor")+COUNTIFS('S4'!$B$6:$B$22,$A11,'S4'!$E$6:$E$22,"Ambos")+COUNTIFS('S5'!$B$6:$B$20,$A11,'S5'!$E$6:$E$20,"Víctor")+COUNTIFS('S5'!$B$6:$B$20,$A11,'S5'!$E$6:$E$20,"Ambos")+COUNTIFS('S6'!$B$6:$B$17,$A11,'S6'!$E$6:$E$17,"Víctor")+COUNTIFS('S6'!$B$6:$B$17,$A11,'S6'!$E$6:$E$17,"Ambos")+COUNTIFS('S7'!$B$6:$B$19,$A11,'S7'!$E$6:$E$19,"Víctor")+COUNTIFS('S7'!$B$6:$B$19,$A11,'S7'!$E$6:$E$19,"Ambos")+COUNTIFS('S8'!$B$6:$B$23,$A11,'S8'!$E$6:$E$23,"Víctor")+COUNTIFS('S8'!$B$6:$B$23,$A11,'S8'!$E$6:$E$23,"Ambos")+COUNTIFS('S9'!$B$6:$B$15,$A11,'S9'!$E$6:$E$15,"Víctor")+COUNTIFS('S9'!$B$6:$B$15,$A11,'S9'!$E$6:$E$15,"Ambos")+COUNTIFS('S10'!$B$6:$B$13,$A11,'S10'!$E$6:$E$13,"Víctor")+COUNTIFS('S10'!$B$6:$B$13,$A11,'S10'!$E$6:$E$13,"Ambos")+COUNTIFS('Holgura'!$B$6:$B$11,$A11,'Holgura'!$E$6:$E$11,"Víctor")+COUNTIFS('Holgura'!$B$6:$B$11,$A11,'Holgura'!$E$6:$E$11,"Ambos")+COUNTIFS('Entrega'!$B$6:$B$9,$A11,'Entrega'!$E$6:$E$9,"Víctor")+COUNTIFS('Entrega'!$B$6:$B$9,$A11,'Entrega'!$E$6:$E$9,"Ambos")+COUNTIFS('Defensa'!$B$6:$B$10,$A11,'Defensa'!$E$6:$E$10,"Víctor")+COUNTIFS('Defensa'!$B$6:$B$10,$A11,'Defensa'!$E$6:$E$10,"Ambos")</f>
         <v/>
       </c>
       <c r="G11" s="21">
-        <f>COUNTIFS('S1'!$B$6:$B$32,$A11,'S1'!$E$6:$E$32,"Diego")+COUNTIFS('S1'!$B$6:$B$32,$A11,'S1'!$E$6:$E$32,"Ambos")+COUNTIFS('S2'!$B$6:$B$23,$A11,'S2'!$E$6:$E$23,"Diego")+COUNTIFS('S2'!$B$6:$B$23,$A11,'S2'!$E$6:$E$23,"Ambos")+COUNTIFS('S3'!$B$6:$B$19,$A11,'S3'!$E$6:$E$19,"Diego")+COUNTIFS('S3'!$B$6:$B$19,$A11,'S3'!$E$6:$E$19,"Ambos")+COUNTIFS('S4'!$B$6:$B$20,$A11,'S4'!$E$6:$E$20,"Diego")+COUNTIFS('S4'!$B$6:$B$20,$A11,'S4'!$E$6:$E$20,"Ambos")+COUNTIFS('S5'!$B$6:$B$20,$A11,'S5'!$E$6:$E$20,"Diego")+COUNTIFS('S5'!$B$6:$B$20,$A11,'S5'!$E$6:$E$20,"Ambos")+COUNTIFS('S6'!$B$6:$B$17,$A11,'S6'!$E$6:$E$17,"Diego")+COUNTIFS('S6'!$B$6:$B$17,$A11,'S6'!$E$6:$E$17,"Ambos")+COUNTIFS('S7'!$B$6:$B$19,$A11,'S7'!$E$6:$E$19,"Diego")+COUNTIFS('S7'!$B$6:$B$19,$A11,'S7'!$E$6:$E$19,"Ambos")+COUNTIFS('S8'!$B$6:$B$23,$A11,'S8'!$E$6:$E$23,"Diego")+COUNTIFS('S8'!$B$6:$B$23,$A11,'S8'!$E$6:$E$23,"Ambos")+COUNTIFS('S9'!$B$6:$B$15,$A11,'S9'!$E$6:$E$15,"Diego")+COUNTIFS('S9'!$B$6:$B$15,$A11,'S9'!$E$6:$E$15,"Ambos")+COUNTIFS('S10'!$B$6:$B$13,$A11,'S10'!$E$6:$E$13,"Diego")+COUNTIFS('S10'!$B$6:$B$13,$A11,'S10'!$E$6:$E$13,"Ambos")+COUNTIFS('Holgura'!$B$6:$B$11,$A11,'Holgura'!$E$6:$E$11,"Diego")+COUNTIFS('Holgura'!$B$6:$B$11,$A11,'Holgura'!$E$6:$E$11,"Ambos")+COUNTIFS('Entrega'!$B$6:$B$9,$A11,'Entrega'!$E$6:$E$9,"Diego")+COUNTIFS('Entrega'!$B$6:$B$9,$A11,'Entrega'!$E$6:$E$9,"Ambos")+COUNTIFS('Defensa'!$B$6:$B$10,$A11,'Defensa'!$E$6:$E$10,"Diego")+COUNTIFS('Defensa'!$B$6:$B$10,$A11,'Defensa'!$E$6:$E$10,"Ambos")</f>
+        <f>COUNTIFS('S1'!$B$6:$B$32,$A11,'S1'!$E$6:$E$32,"Diego")+COUNTIFS('S1'!$B$6:$B$32,$A11,'S1'!$E$6:$E$32,"Ambos")+COUNTIFS('S2'!$B$6:$B$23,$A11,'S2'!$E$6:$E$23,"Diego")+COUNTIFS('S2'!$B$6:$B$23,$A11,'S2'!$E$6:$E$23,"Ambos")+COUNTIFS('S3'!$B$6:$B$24,$A11,'S3'!$E$6:$E$24,"Diego")+COUNTIFS('S3'!$B$6:$B$24,$A11,'S3'!$E$6:$E$24,"Ambos")+COUNTIFS('S4'!$B$6:$B$22,$A11,'S4'!$E$6:$E$22,"Diego")+COUNTIFS('S4'!$B$6:$B$22,$A11,'S4'!$E$6:$E$22,"Ambos")+COUNTIFS('S5'!$B$6:$B$20,$A11,'S5'!$E$6:$E$20,"Diego")+COUNTIFS('S5'!$B$6:$B$20,$A11,'S5'!$E$6:$E$20,"Ambos")+COUNTIFS('S6'!$B$6:$B$17,$A11,'S6'!$E$6:$E$17,"Diego")+COUNTIFS('S6'!$B$6:$B$17,$A11,'S6'!$E$6:$E$17,"Ambos")+COUNTIFS('S7'!$B$6:$B$19,$A11,'S7'!$E$6:$E$19,"Diego")+COUNTIFS('S7'!$B$6:$B$19,$A11,'S7'!$E$6:$E$19,"Ambos")+COUNTIFS('S8'!$B$6:$B$23,$A11,'S8'!$E$6:$E$23,"Diego")+COUNTIFS('S8'!$B$6:$B$23,$A11,'S8'!$E$6:$E$23,"Ambos")+COUNTIFS('S9'!$B$6:$B$15,$A11,'S9'!$E$6:$E$15,"Diego")+COUNTIFS('S9'!$B$6:$B$15,$A11,'S9'!$E$6:$E$15,"Ambos")+COUNTIFS('S10'!$B$6:$B$13,$A11,'S10'!$E$6:$E$13,"Diego")+COUNTIFS('S10'!$B$6:$B$13,$A11,'S10'!$E$6:$E$13,"Ambos")+COUNTIFS('Holgura'!$B$6:$B$11,$A11,'Holgura'!$E$6:$E$11,"Diego")+COUNTIFS('Holgura'!$B$6:$B$11,$A11,'Holgura'!$E$6:$E$11,"Ambos")+COUNTIFS('Entrega'!$B$6:$B$9,$A11,'Entrega'!$E$6:$E$9,"Diego")+COUNTIFS('Entrega'!$B$6:$B$9,$A11,'Entrega'!$E$6:$E$9,"Ambos")+COUNTIFS('Defensa'!$B$6:$B$10,$A11,'Defensa'!$E$6:$E$10,"Diego")+COUNTIFS('Defensa'!$B$6:$B$10,$A11,'Defensa'!$E$6:$E$10,"Ambos")</f>
         <v/>
       </c>
     </row>
@@ -8883,19 +8904,19 @@
         <v/>
       </c>
       <c r="D12" s="21">
-        <f>SUMIFS('S1'!$I$6:$I$32,'S1'!$B$6:$B$32,$A12,'S1'!$E$6:$E$32,"Víctor")+SUMIFS('S1'!$I$6:$I$32,'S1'!$B$6:$B$32,$A12,'S1'!$E$6:$E$32,"Ambos")+SUMIFS('S2'!$I$6:$I$23,'S2'!$B$6:$B$23,$A12,'S2'!$E$6:$E$23,"Víctor")+SUMIFS('S2'!$I$6:$I$23,'S2'!$B$6:$B$23,$A12,'S2'!$E$6:$E$23,"Ambos")+SUMIFS('S3'!$I$6:$I$19,'S3'!$B$6:$B$19,$A12,'S3'!$E$6:$E$19,"Víctor")+SUMIFS('S3'!$I$6:$I$19,'S3'!$B$6:$B$19,$A12,'S3'!$E$6:$E$19,"Ambos")+SUMIFS('S4'!$I$6:$I$20,'S4'!$B$6:$B$20,$A12,'S4'!$E$6:$E$20,"Víctor")+SUMIFS('S4'!$I$6:$I$20,'S4'!$B$6:$B$20,$A12,'S4'!$E$6:$E$20,"Ambos")+SUMIFS('S5'!$I$6:$I$20,'S5'!$B$6:$B$20,$A12,'S5'!$E$6:$E$20,"Víctor")+SUMIFS('S5'!$I$6:$I$20,'S5'!$B$6:$B$20,$A12,'S5'!$E$6:$E$20,"Ambos")+SUMIFS('S6'!$I$6:$I$17,'S6'!$B$6:$B$17,$A12,'S6'!$E$6:$E$17,"Víctor")+SUMIFS('S6'!$I$6:$I$17,'S6'!$B$6:$B$17,$A12,'S6'!$E$6:$E$17,"Ambos")+SUMIFS('S7'!$I$6:$I$19,'S7'!$B$6:$B$19,$A12,'S7'!$E$6:$E$19,"Víctor")+SUMIFS('S7'!$I$6:$I$19,'S7'!$B$6:$B$19,$A12,'S7'!$E$6:$E$19,"Ambos")+SUMIFS('S8'!$I$6:$I$23,'S8'!$B$6:$B$23,$A12,'S8'!$E$6:$E$23,"Víctor")+SUMIFS('S8'!$I$6:$I$23,'S8'!$B$6:$B$23,$A12,'S8'!$E$6:$E$23,"Ambos")+SUMIFS('S9'!$I$6:$I$15,'S9'!$B$6:$B$15,$A12,'S9'!$E$6:$E$15,"Víctor")+SUMIFS('S9'!$I$6:$I$15,'S9'!$B$6:$B$15,$A12,'S9'!$E$6:$E$15,"Ambos")+SUMIFS('S10'!$I$6:$I$13,'S10'!$B$6:$B$13,$A12,'S10'!$E$6:$E$13,"Víctor")+SUMIFS('S10'!$I$6:$I$13,'S10'!$B$6:$B$13,$A12,'S10'!$E$6:$E$13,"Ambos")+SUMIFS('Holgura'!$I$6:$I$11,'Holgura'!$B$6:$B$11,$A12,'Holgura'!$E$6:$E$11,"Víctor")+SUMIFS('Holgura'!$I$6:$I$11,'Holgura'!$B$6:$B$11,$A12,'Holgura'!$E$6:$E$11,"Ambos")+SUMIFS('Entrega'!$I$6:$I$9,'Entrega'!$B$6:$B$9,$A12,'Entrega'!$E$6:$E$9,"Víctor")+SUMIFS('Entrega'!$I$6:$I$9,'Entrega'!$B$6:$B$9,$A12,'Entrega'!$E$6:$E$9,"Ambos")+SUMIFS('Defensa'!$I$6:$I$10,'Defensa'!$B$6:$B$10,$A12,'Defensa'!$E$6:$E$10,"Víctor")+SUMIFS('Defensa'!$I$6:$I$10,'Defensa'!$B$6:$B$10,$A12,'Defensa'!$E$6:$E$10,"Ambos")</f>
+        <f>SUMIFS('S1'!$I$6:$I$32,'S1'!$B$6:$B$32,$A12,'S1'!$E$6:$E$32,"Víctor")+SUMIFS('S1'!$I$6:$I$32,'S1'!$B$6:$B$32,$A12,'S1'!$E$6:$E$32,"Ambos")+SUMIFS('S2'!$I$6:$I$23,'S2'!$B$6:$B$23,$A12,'S2'!$E$6:$E$23,"Víctor")+SUMIFS('S2'!$I$6:$I$23,'S2'!$B$6:$B$23,$A12,'S2'!$E$6:$E$23,"Ambos")+SUMIFS('S3'!$I$6:$I$24,'S3'!$B$6:$B$24,$A12,'S3'!$E$6:$E$24,"Víctor")+SUMIFS('S3'!$I$6:$I$24,'S3'!$B$6:$B$24,$A12,'S3'!$E$6:$E$24,"Ambos")+SUMIFS('S4'!$I$6:$I$22,'S4'!$B$6:$B$22,$A12,'S4'!$E$6:$E$22,"Víctor")+SUMIFS('S4'!$I$6:$I$22,'S4'!$B$6:$B$22,$A12,'S4'!$E$6:$E$22,"Ambos")+SUMIFS('S5'!$I$6:$I$20,'S5'!$B$6:$B$20,$A12,'S5'!$E$6:$E$20,"Víctor")+SUMIFS('S5'!$I$6:$I$20,'S5'!$B$6:$B$20,$A12,'S5'!$E$6:$E$20,"Ambos")+SUMIFS('S6'!$I$6:$I$17,'S6'!$B$6:$B$17,$A12,'S6'!$E$6:$E$17,"Víctor")+SUMIFS('S6'!$I$6:$I$17,'S6'!$B$6:$B$17,$A12,'S6'!$E$6:$E$17,"Ambos")+SUMIFS('S7'!$I$6:$I$19,'S7'!$B$6:$B$19,$A12,'S7'!$E$6:$E$19,"Víctor")+SUMIFS('S7'!$I$6:$I$19,'S7'!$B$6:$B$19,$A12,'S7'!$E$6:$E$19,"Ambos")+SUMIFS('S8'!$I$6:$I$23,'S8'!$B$6:$B$23,$A12,'S8'!$E$6:$E$23,"Víctor")+SUMIFS('S8'!$I$6:$I$23,'S8'!$B$6:$B$23,$A12,'S8'!$E$6:$E$23,"Ambos")+SUMIFS('S9'!$I$6:$I$15,'S9'!$B$6:$B$15,$A12,'S9'!$E$6:$E$15,"Víctor")+SUMIFS('S9'!$I$6:$I$15,'S9'!$B$6:$B$15,$A12,'S9'!$E$6:$E$15,"Ambos")+SUMIFS('S10'!$I$6:$I$13,'S10'!$B$6:$B$13,$A12,'S10'!$E$6:$E$13,"Víctor")+SUMIFS('S10'!$I$6:$I$13,'S10'!$B$6:$B$13,$A12,'S10'!$E$6:$E$13,"Ambos")+SUMIFS('Holgura'!$I$6:$I$11,'Holgura'!$B$6:$B$11,$A12,'Holgura'!$E$6:$E$11,"Víctor")+SUMIFS('Holgura'!$I$6:$I$11,'Holgura'!$B$6:$B$11,$A12,'Holgura'!$E$6:$E$11,"Ambos")+SUMIFS('Entrega'!$I$6:$I$9,'Entrega'!$B$6:$B$9,$A12,'Entrega'!$E$6:$E$9,"Víctor")+SUMIFS('Entrega'!$I$6:$I$9,'Entrega'!$B$6:$B$9,$A12,'Entrega'!$E$6:$E$9,"Ambos")+SUMIFS('Defensa'!$I$6:$I$10,'Defensa'!$B$6:$B$10,$A12,'Defensa'!$E$6:$E$10,"Víctor")+SUMIFS('Defensa'!$I$6:$I$10,'Defensa'!$B$6:$B$10,$A12,'Defensa'!$E$6:$E$10,"Ambos")</f>
         <v/>
       </c>
       <c r="E12" s="21">
-        <f>SUMIFS('S1'!$I$6:$I$32,'S1'!$B$6:$B$32,$A12,'S1'!$E$6:$E$32,"Diego")+SUMIFS('S1'!$I$6:$I$32,'S1'!$B$6:$B$32,$A12,'S1'!$E$6:$E$32,"Ambos")+SUMIFS('S2'!$I$6:$I$23,'S2'!$B$6:$B$23,$A12,'S2'!$E$6:$E$23,"Diego")+SUMIFS('S2'!$I$6:$I$23,'S2'!$B$6:$B$23,$A12,'S2'!$E$6:$E$23,"Ambos")+SUMIFS('S3'!$I$6:$I$19,'S3'!$B$6:$B$19,$A12,'S3'!$E$6:$E$19,"Diego")+SUMIFS('S3'!$I$6:$I$19,'S3'!$B$6:$B$19,$A12,'S3'!$E$6:$E$19,"Ambos")+SUMIFS('S4'!$I$6:$I$20,'S4'!$B$6:$B$20,$A12,'S4'!$E$6:$E$20,"Diego")+SUMIFS('S4'!$I$6:$I$20,'S4'!$B$6:$B$20,$A12,'S4'!$E$6:$E$20,"Ambos")+SUMIFS('S5'!$I$6:$I$20,'S5'!$B$6:$B$20,$A12,'S5'!$E$6:$E$20,"Diego")+SUMIFS('S5'!$I$6:$I$20,'S5'!$B$6:$B$20,$A12,'S5'!$E$6:$E$20,"Ambos")+SUMIFS('S6'!$I$6:$I$17,'S6'!$B$6:$B$17,$A12,'S6'!$E$6:$E$17,"Diego")+SUMIFS('S6'!$I$6:$I$17,'S6'!$B$6:$B$17,$A12,'S6'!$E$6:$E$17,"Ambos")+SUMIFS('S7'!$I$6:$I$19,'S7'!$B$6:$B$19,$A12,'S7'!$E$6:$E$19,"Diego")+SUMIFS('S7'!$I$6:$I$19,'S7'!$B$6:$B$19,$A12,'S7'!$E$6:$E$19,"Ambos")+SUMIFS('S8'!$I$6:$I$23,'S8'!$B$6:$B$23,$A12,'S8'!$E$6:$E$23,"Diego")+SUMIFS('S8'!$I$6:$I$23,'S8'!$B$6:$B$23,$A12,'S8'!$E$6:$E$23,"Ambos")+SUMIFS('S9'!$I$6:$I$15,'S9'!$B$6:$B$15,$A12,'S9'!$E$6:$E$15,"Diego")+SUMIFS('S9'!$I$6:$I$15,'S9'!$B$6:$B$15,$A12,'S9'!$E$6:$E$15,"Ambos")+SUMIFS('S10'!$I$6:$I$13,'S10'!$B$6:$B$13,$A12,'S10'!$E$6:$E$13,"Diego")+SUMIFS('S10'!$I$6:$I$13,'S10'!$B$6:$B$13,$A12,'S10'!$E$6:$E$13,"Ambos")+SUMIFS('Holgura'!$I$6:$I$11,'Holgura'!$B$6:$B$11,$A12,'Holgura'!$E$6:$E$11,"Diego")+SUMIFS('Holgura'!$I$6:$I$11,'Holgura'!$B$6:$B$11,$A12,'Holgura'!$E$6:$E$11,"Ambos")+SUMIFS('Entrega'!$I$6:$I$9,'Entrega'!$B$6:$B$9,$A12,'Entrega'!$E$6:$E$9,"Diego")+SUMIFS('Entrega'!$I$6:$I$9,'Entrega'!$B$6:$B$9,$A12,'Entrega'!$E$6:$E$9,"Ambos")+SUMIFS('Defensa'!$I$6:$I$10,'Defensa'!$B$6:$B$10,$A12,'Defensa'!$E$6:$E$10,"Diego")+SUMIFS('Defensa'!$I$6:$I$10,'Defensa'!$B$6:$B$10,$A12,'Defensa'!$E$6:$E$10,"Ambos")</f>
+        <f>SUMIFS('S1'!$I$6:$I$32,'S1'!$B$6:$B$32,$A12,'S1'!$E$6:$E$32,"Diego")+SUMIFS('S1'!$I$6:$I$32,'S1'!$B$6:$B$32,$A12,'S1'!$E$6:$E$32,"Ambos")+SUMIFS('S2'!$I$6:$I$23,'S2'!$B$6:$B$23,$A12,'S2'!$E$6:$E$23,"Diego")+SUMIFS('S2'!$I$6:$I$23,'S2'!$B$6:$B$23,$A12,'S2'!$E$6:$E$23,"Ambos")+SUMIFS('S3'!$I$6:$I$24,'S3'!$B$6:$B$24,$A12,'S3'!$E$6:$E$24,"Diego")+SUMIFS('S3'!$I$6:$I$24,'S3'!$B$6:$B$24,$A12,'S3'!$E$6:$E$24,"Ambos")+SUMIFS('S4'!$I$6:$I$22,'S4'!$B$6:$B$22,$A12,'S4'!$E$6:$E$22,"Diego")+SUMIFS('S4'!$I$6:$I$22,'S4'!$B$6:$B$22,$A12,'S4'!$E$6:$E$22,"Ambos")+SUMIFS('S5'!$I$6:$I$20,'S5'!$B$6:$B$20,$A12,'S5'!$E$6:$E$20,"Diego")+SUMIFS('S5'!$I$6:$I$20,'S5'!$B$6:$B$20,$A12,'S5'!$E$6:$E$20,"Ambos")+SUMIFS('S6'!$I$6:$I$17,'S6'!$B$6:$B$17,$A12,'S6'!$E$6:$E$17,"Diego")+SUMIFS('S6'!$I$6:$I$17,'S6'!$B$6:$B$17,$A12,'S6'!$E$6:$E$17,"Ambos")+SUMIFS('S7'!$I$6:$I$19,'S7'!$B$6:$B$19,$A12,'S7'!$E$6:$E$19,"Diego")+SUMIFS('S7'!$I$6:$I$19,'S7'!$B$6:$B$19,$A12,'S7'!$E$6:$E$19,"Ambos")+SUMIFS('S8'!$I$6:$I$23,'S8'!$B$6:$B$23,$A12,'S8'!$E$6:$E$23,"Diego")+SUMIFS('S8'!$I$6:$I$23,'S8'!$B$6:$B$23,$A12,'S8'!$E$6:$E$23,"Ambos")+SUMIFS('S9'!$I$6:$I$15,'S9'!$B$6:$B$15,$A12,'S9'!$E$6:$E$15,"Diego")+SUMIFS('S9'!$I$6:$I$15,'S9'!$B$6:$B$15,$A12,'S9'!$E$6:$E$15,"Ambos")+SUMIFS('S10'!$I$6:$I$13,'S10'!$B$6:$B$13,$A12,'S10'!$E$6:$E$13,"Diego")+SUMIFS('S10'!$I$6:$I$13,'S10'!$B$6:$B$13,$A12,'S10'!$E$6:$E$13,"Ambos")+SUMIFS('Holgura'!$I$6:$I$11,'Holgura'!$B$6:$B$11,$A12,'Holgura'!$E$6:$E$11,"Diego")+SUMIFS('Holgura'!$I$6:$I$11,'Holgura'!$B$6:$B$11,$A12,'Holgura'!$E$6:$E$11,"Ambos")+SUMIFS('Entrega'!$I$6:$I$9,'Entrega'!$B$6:$B$9,$A12,'Entrega'!$E$6:$E$9,"Diego")+SUMIFS('Entrega'!$I$6:$I$9,'Entrega'!$B$6:$B$9,$A12,'Entrega'!$E$6:$E$9,"Ambos")+SUMIFS('Defensa'!$I$6:$I$10,'Defensa'!$B$6:$B$10,$A12,'Defensa'!$E$6:$E$10,"Diego")+SUMIFS('Defensa'!$I$6:$I$10,'Defensa'!$B$6:$B$10,$A12,'Defensa'!$E$6:$E$10,"Ambos")</f>
         <v/>
       </c>
       <c r="F12" s="21">
-        <f>COUNTIFS('S1'!$B$6:$B$32,$A12,'S1'!$E$6:$E$32,"Víctor")+COUNTIFS('S1'!$B$6:$B$32,$A12,'S1'!$E$6:$E$32,"Ambos")+COUNTIFS('S2'!$B$6:$B$23,$A12,'S2'!$E$6:$E$23,"Víctor")+COUNTIFS('S2'!$B$6:$B$23,$A12,'S2'!$E$6:$E$23,"Ambos")+COUNTIFS('S3'!$B$6:$B$19,$A12,'S3'!$E$6:$E$19,"Víctor")+COUNTIFS('S3'!$B$6:$B$19,$A12,'S3'!$E$6:$E$19,"Ambos")+COUNTIFS('S4'!$B$6:$B$20,$A12,'S4'!$E$6:$E$20,"Víctor")+COUNTIFS('S4'!$B$6:$B$20,$A12,'S4'!$E$6:$E$20,"Ambos")+COUNTIFS('S5'!$B$6:$B$20,$A12,'S5'!$E$6:$E$20,"Víctor")+COUNTIFS('S5'!$B$6:$B$20,$A12,'S5'!$E$6:$E$20,"Ambos")+COUNTIFS('S6'!$B$6:$B$17,$A12,'S6'!$E$6:$E$17,"Víctor")+COUNTIFS('S6'!$B$6:$B$17,$A12,'S6'!$E$6:$E$17,"Ambos")+COUNTIFS('S7'!$B$6:$B$19,$A12,'S7'!$E$6:$E$19,"Víctor")+COUNTIFS('S7'!$B$6:$B$19,$A12,'S7'!$E$6:$E$19,"Ambos")+COUNTIFS('S8'!$B$6:$B$23,$A12,'S8'!$E$6:$E$23,"Víctor")+COUNTIFS('S8'!$B$6:$B$23,$A12,'S8'!$E$6:$E$23,"Ambos")+COUNTIFS('S9'!$B$6:$B$15,$A12,'S9'!$E$6:$E$15,"Víctor")+COUNTIFS('S9'!$B$6:$B$15,$A12,'S9'!$E$6:$E$15,"Ambos")+COUNTIFS('S10'!$B$6:$B$13,$A12,'S10'!$E$6:$E$13,"Víctor")+COUNTIFS('S10'!$B$6:$B$13,$A12,'S10'!$E$6:$E$13,"Ambos")+COUNTIFS('Holgura'!$B$6:$B$11,$A12,'Holgura'!$E$6:$E$11,"Víctor")+COUNTIFS('Holgura'!$B$6:$B$11,$A12,'Holgura'!$E$6:$E$11,"Ambos")+COUNTIFS('Entrega'!$B$6:$B$9,$A12,'Entrega'!$E$6:$E$9,"Víctor")+COUNTIFS('Entrega'!$B$6:$B$9,$A12,'Entrega'!$E$6:$E$9,"Ambos")+COUNTIFS('Defensa'!$B$6:$B$10,$A12,'Defensa'!$E$6:$E$10,"Víctor")+COUNTIFS('Defensa'!$B$6:$B$10,$A12,'Defensa'!$E$6:$E$10,"Ambos")</f>
+        <f>COUNTIFS('S1'!$B$6:$B$32,$A12,'S1'!$E$6:$E$32,"Víctor")+COUNTIFS('S1'!$B$6:$B$32,$A12,'S1'!$E$6:$E$32,"Ambos")+COUNTIFS('S2'!$B$6:$B$23,$A12,'S2'!$E$6:$E$23,"Víctor")+COUNTIFS('S2'!$B$6:$B$23,$A12,'S2'!$E$6:$E$23,"Ambos")+COUNTIFS('S3'!$B$6:$B$24,$A12,'S3'!$E$6:$E$24,"Víctor")+COUNTIFS('S3'!$B$6:$B$24,$A12,'S3'!$E$6:$E$24,"Ambos")+COUNTIFS('S4'!$B$6:$B$22,$A12,'S4'!$E$6:$E$22,"Víctor")+COUNTIFS('S4'!$B$6:$B$22,$A12,'S4'!$E$6:$E$22,"Ambos")+COUNTIFS('S5'!$B$6:$B$20,$A12,'S5'!$E$6:$E$20,"Víctor")+COUNTIFS('S5'!$B$6:$B$20,$A12,'S5'!$E$6:$E$20,"Ambos")+COUNTIFS('S6'!$B$6:$B$17,$A12,'S6'!$E$6:$E$17,"Víctor")+COUNTIFS('S6'!$B$6:$B$17,$A12,'S6'!$E$6:$E$17,"Ambos")+COUNTIFS('S7'!$B$6:$B$19,$A12,'S7'!$E$6:$E$19,"Víctor")+COUNTIFS('S7'!$B$6:$B$19,$A12,'S7'!$E$6:$E$19,"Ambos")+COUNTIFS('S8'!$B$6:$B$23,$A12,'S8'!$E$6:$E$23,"Víctor")+COUNTIFS('S8'!$B$6:$B$23,$A12,'S8'!$E$6:$E$23,"Ambos")+COUNTIFS('S9'!$B$6:$B$15,$A12,'S9'!$E$6:$E$15,"Víctor")+COUNTIFS('S9'!$B$6:$B$15,$A12,'S9'!$E$6:$E$15,"Ambos")+COUNTIFS('S10'!$B$6:$B$13,$A12,'S10'!$E$6:$E$13,"Víctor")+COUNTIFS('S10'!$B$6:$B$13,$A12,'S10'!$E$6:$E$13,"Ambos")+COUNTIFS('Holgura'!$B$6:$B$11,$A12,'Holgura'!$E$6:$E$11,"Víctor")+COUNTIFS('Holgura'!$B$6:$B$11,$A12,'Holgura'!$E$6:$E$11,"Ambos")+COUNTIFS('Entrega'!$B$6:$B$9,$A12,'Entrega'!$E$6:$E$9,"Víctor")+COUNTIFS('Entrega'!$B$6:$B$9,$A12,'Entrega'!$E$6:$E$9,"Ambos")+COUNTIFS('Defensa'!$B$6:$B$10,$A12,'Defensa'!$E$6:$E$10,"Víctor")+COUNTIFS('Defensa'!$B$6:$B$10,$A12,'Defensa'!$E$6:$E$10,"Ambos")</f>
         <v/>
       </c>
       <c r="G12" s="21">
-        <f>COUNTIFS('S1'!$B$6:$B$32,$A12,'S1'!$E$6:$E$32,"Diego")+COUNTIFS('S1'!$B$6:$B$32,$A12,'S1'!$E$6:$E$32,"Ambos")+COUNTIFS('S2'!$B$6:$B$23,$A12,'S2'!$E$6:$E$23,"Diego")+COUNTIFS('S2'!$B$6:$B$23,$A12,'S2'!$E$6:$E$23,"Ambos")+COUNTIFS('S3'!$B$6:$B$19,$A12,'S3'!$E$6:$E$19,"Diego")+COUNTIFS('S3'!$B$6:$B$19,$A12,'S3'!$E$6:$E$19,"Ambos")+COUNTIFS('S4'!$B$6:$B$20,$A12,'S4'!$E$6:$E$20,"Diego")+COUNTIFS('S4'!$B$6:$B$20,$A12,'S4'!$E$6:$E$20,"Ambos")+COUNTIFS('S5'!$B$6:$B$20,$A12,'S5'!$E$6:$E$20,"Diego")+COUNTIFS('S5'!$B$6:$B$20,$A12,'S5'!$E$6:$E$20,"Ambos")+COUNTIFS('S6'!$B$6:$B$17,$A12,'S6'!$E$6:$E$17,"Diego")+COUNTIFS('S6'!$B$6:$B$17,$A12,'S6'!$E$6:$E$17,"Ambos")+COUNTIFS('S7'!$B$6:$B$19,$A12,'S7'!$E$6:$E$19,"Diego")+COUNTIFS('S7'!$B$6:$B$19,$A12,'S7'!$E$6:$E$19,"Ambos")+COUNTIFS('S8'!$B$6:$B$23,$A12,'S8'!$E$6:$E$23,"Diego")+COUNTIFS('S8'!$B$6:$B$23,$A12,'S8'!$E$6:$E$23,"Ambos")+COUNTIFS('S9'!$B$6:$B$15,$A12,'S9'!$E$6:$E$15,"Diego")+COUNTIFS('S9'!$B$6:$B$15,$A12,'S9'!$E$6:$E$15,"Ambos")+COUNTIFS('S10'!$B$6:$B$13,$A12,'S10'!$E$6:$E$13,"Diego")+COUNTIFS('S10'!$B$6:$B$13,$A12,'S10'!$E$6:$E$13,"Ambos")+COUNTIFS('Holgura'!$B$6:$B$11,$A12,'Holgura'!$E$6:$E$11,"Diego")+COUNTIFS('Holgura'!$B$6:$B$11,$A12,'Holgura'!$E$6:$E$11,"Ambos")+COUNTIFS('Entrega'!$B$6:$B$9,$A12,'Entrega'!$E$6:$E$9,"Diego")+COUNTIFS('Entrega'!$B$6:$B$9,$A12,'Entrega'!$E$6:$E$9,"Ambos")+COUNTIFS('Defensa'!$B$6:$B$10,$A12,'Defensa'!$E$6:$E$10,"Diego")+COUNTIFS('Defensa'!$B$6:$B$10,$A12,'Defensa'!$E$6:$E$10,"Ambos")</f>
+        <f>COUNTIFS('S1'!$B$6:$B$32,$A12,'S1'!$E$6:$E$32,"Diego")+COUNTIFS('S1'!$B$6:$B$32,$A12,'S1'!$E$6:$E$32,"Ambos")+COUNTIFS('S2'!$B$6:$B$23,$A12,'S2'!$E$6:$E$23,"Diego")+COUNTIFS('S2'!$B$6:$B$23,$A12,'S2'!$E$6:$E$23,"Ambos")+COUNTIFS('S3'!$B$6:$B$24,$A12,'S3'!$E$6:$E$24,"Diego")+COUNTIFS('S3'!$B$6:$B$24,$A12,'S3'!$E$6:$E$24,"Ambos")+COUNTIFS('S4'!$B$6:$B$22,$A12,'S4'!$E$6:$E$22,"Diego")+COUNTIFS('S4'!$B$6:$B$22,$A12,'S4'!$E$6:$E$22,"Ambos")+COUNTIFS('S5'!$B$6:$B$20,$A12,'S5'!$E$6:$E$20,"Diego")+COUNTIFS('S5'!$B$6:$B$20,$A12,'S5'!$E$6:$E$20,"Ambos")+COUNTIFS('S6'!$B$6:$B$17,$A12,'S6'!$E$6:$E$17,"Diego")+COUNTIFS('S6'!$B$6:$B$17,$A12,'S6'!$E$6:$E$17,"Ambos")+COUNTIFS('S7'!$B$6:$B$19,$A12,'S7'!$E$6:$E$19,"Diego")+COUNTIFS('S7'!$B$6:$B$19,$A12,'S7'!$E$6:$E$19,"Ambos")+COUNTIFS('S8'!$B$6:$B$23,$A12,'S8'!$E$6:$E$23,"Diego")+COUNTIFS('S8'!$B$6:$B$23,$A12,'S8'!$E$6:$E$23,"Ambos")+COUNTIFS('S9'!$B$6:$B$15,$A12,'S9'!$E$6:$E$15,"Diego")+COUNTIFS('S9'!$B$6:$B$15,$A12,'S9'!$E$6:$E$15,"Ambos")+COUNTIFS('S10'!$B$6:$B$13,$A12,'S10'!$E$6:$E$13,"Diego")+COUNTIFS('S10'!$B$6:$B$13,$A12,'S10'!$E$6:$E$13,"Ambos")+COUNTIFS('Holgura'!$B$6:$B$11,$A12,'Holgura'!$E$6:$E$11,"Diego")+COUNTIFS('Holgura'!$B$6:$B$11,$A12,'Holgura'!$E$6:$E$11,"Ambos")+COUNTIFS('Entrega'!$B$6:$B$9,$A12,'Entrega'!$E$6:$E$9,"Diego")+COUNTIFS('Entrega'!$B$6:$B$9,$A12,'Entrega'!$E$6:$E$9,"Ambos")+COUNTIFS('Defensa'!$B$6:$B$10,$A12,'Defensa'!$E$6:$E$10,"Diego")+COUNTIFS('Defensa'!$B$6:$B$10,$A12,'Defensa'!$E$6:$E$10,"Ambos")</f>
         <v/>
       </c>
     </row>
@@ -8912,19 +8933,19 @@
         <v/>
       </c>
       <c r="D13" s="21">
-        <f>SUMIFS('S1'!$I$6:$I$32,'S1'!$B$6:$B$32,$A13,'S1'!$E$6:$E$32,"Víctor")+SUMIFS('S1'!$I$6:$I$32,'S1'!$B$6:$B$32,$A13,'S1'!$E$6:$E$32,"Ambos")+SUMIFS('S2'!$I$6:$I$23,'S2'!$B$6:$B$23,$A13,'S2'!$E$6:$E$23,"Víctor")+SUMIFS('S2'!$I$6:$I$23,'S2'!$B$6:$B$23,$A13,'S2'!$E$6:$E$23,"Ambos")+SUMIFS('S3'!$I$6:$I$19,'S3'!$B$6:$B$19,$A13,'S3'!$E$6:$E$19,"Víctor")+SUMIFS('S3'!$I$6:$I$19,'S3'!$B$6:$B$19,$A13,'S3'!$E$6:$E$19,"Ambos")+SUMIFS('S4'!$I$6:$I$20,'S4'!$B$6:$B$20,$A13,'S4'!$E$6:$E$20,"Víctor")+SUMIFS('S4'!$I$6:$I$20,'S4'!$B$6:$B$20,$A13,'S4'!$E$6:$E$20,"Ambos")+SUMIFS('S5'!$I$6:$I$20,'S5'!$B$6:$B$20,$A13,'S5'!$E$6:$E$20,"Víctor")+SUMIFS('S5'!$I$6:$I$20,'S5'!$B$6:$B$20,$A13,'S5'!$E$6:$E$20,"Ambos")+SUMIFS('S6'!$I$6:$I$17,'S6'!$B$6:$B$17,$A13,'S6'!$E$6:$E$17,"Víctor")+SUMIFS('S6'!$I$6:$I$17,'S6'!$B$6:$B$17,$A13,'S6'!$E$6:$E$17,"Ambos")+SUMIFS('S7'!$I$6:$I$19,'S7'!$B$6:$B$19,$A13,'S7'!$E$6:$E$19,"Víctor")+SUMIFS('S7'!$I$6:$I$19,'S7'!$B$6:$B$19,$A13,'S7'!$E$6:$E$19,"Ambos")+SUMIFS('S8'!$I$6:$I$23,'S8'!$B$6:$B$23,$A13,'S8'!$E$6:$E$23,"Víctor")+SUMIFS('S8'!$I$6:$I$23,'S8'!$B$6:$B$23,$A13,'S8'!$E$6:$E$23,"Ambos")+SUMIFS('S9'!$I$6:$I$15,'S9'!$B$6:$B$15,$A13,'S9'!$E$6:$E$15,"Víctor")+SUMIFS('S9'!$I$6:$I$15,'S9'!$B$6:$B$15,$A13,'S9'!$E$6:$E$15,"Ambos")+SUMIFS('S10'!$I$6:$I$13,'S10'!$B$6:$B$13,$A13,'S10'!$E$6:$E$13,"Víctor")+SUMIFS('S10'!$I$6:$I$13,'S10'!$B$6:$B$13,$A13,'S10'!$E$6:$E$13,"Ambos")+SUMIFS('Holgura'!$I$6:$I$11,'Holgura'!$B$6:$B$11,$A13,'Holgura'!$E$6:$E$11,"Víctor")+SUMIFS('Holgura'!$I$6:$I$11,'Holgura'!$B$6:$B$11,$A13,'Holgura'!$E$6:$E$11,"Ambos")+SUMIFS('Entrega'!$I$6:$I$9,'Entrega'!$B$6:$B$9,$A13,'Entrega'!$E$6:$E$9,"Víctor")+SUMIFS('Entrega'!$I$6:$I$9,'Entrega'!$B$6:$B$9,$A13,'Entrega'!$E$6:$E$9,"Ambos")+SUMIFS('Defensa'!$I$6:$I$10,'Defensa'!$B$6:$B$10,$A13,'Defensa'!$E$6:$E$10,"Víctor")+SUMIFS('Defensa'!$I$6:$I$10,'Defensa'!$B$6:$B$10,$A13,'Defensa'!$E$6:$E$10,"Ambos")</f>
+        <f>SUMIFS('S1'!$I$6:$I$32,'S1'!$B$6:$B$32,$A13,'S1'!$E$6:$E$32,"Víctor")+SUMIFS('S1'!$I$6:$I$32,'S1'!$B$6:$B$32,$A13,'S1'!$E$6:$E$32,"Ambos")+SUMIFS('S2'!$I$6:$I$23,'S2'!$B$6:$B$23,$A13,'S2'!$E$6:$E$23,"Víctor")+SUMIFS('S2'!$I$6:$I$23,'S2'!$B$6:$B$23,$A13,'S2'!$E$6:$E$23,"Ambos")+SUMIFS('S3'!$I$6:$I$24,'S3'!$B$6:$B$24,$A13,'S3'!$E$6:$E$24,"Víctor")+SUMIFS('S3'!$I$6:$I$24,'S3'!$B$6:$B$24,$A13,'S3'!$E$6:$E$24,"Ambos")+SUMIFS('S4'!$I$6:$I$22,'S4'!$B$6:$B$22,$A13,'S4'!$E$6:$E$22,"Víctor")+SUMIFS('S4'!$I$6:$I$22,'S4'!$B$6:$B$22,$A13,'S4'!$E$6:$E$22,"Ambos")+SUMIFS('S5'!$I$6:$I$20,'S5'!$B$6:$B$20,$A13,'S5'!$E$6:$E$20,"Víctor")+SUMIFS('S5'!$I$6:$I$20,'S5'!$B$6:$B$20,$A13,'S5'!$E$6:$E$20,"Ambos")+SUMIFS('S6'!$I$6:$I$17,'S6'!$B$6:$B$17,$A13,'S6'!$E$6:$E$17,"Víctor")+SUMIFS('S6'!$I$6:$I$17,'S6'!$B$6:$B$17,$A13,'S6'!$E$6:$E$17,"Ambos")+SUMIFS('S7'!$I$6:$I$19,'S7'!$B$6:$B$19,$A13,'S7'!$E$6:$E$19,"Víctor")+SUMIFS('S7'!$I$6:$I$19,'S7'!$B$6:$B$19,$A13,'S7'!$E$6:$E$19,"Ambos")+SUMIFS('S8'!$I$6:$I$23,'S8'!$B$6:$B$23,$A13,'S8'!$E$6:$E$23,"Víctor")+SUMIFS('S8'!$I$6:$I$23,'S8'!$B$6:$B$23,$A13,'S8'!$E$6:$E$23,"Ambos")+SUMIFS('S9'!$I$6:$I$15,'S9'!$B$6:$B$15,$A13,'S9'!$E$6:$E$15,"Víctor")+SUMIFS('S9'!$I$6:$I$15,'S9'!$B$6:$B$15,$A13,'S9'!$E$6:$E$15,"Ambos")+SUMIFS('S10'!$I$6:$I$13,'S10'!$B$6:$B$13,$A13,'S10'!$E$6:$E$13,"Víctor")+SUMIFS('S10'!$I$6:$I$13,'S10'!$B$6:$B$13,$A13,'S10'!$E$6:$E$13,"Ambos")+SUMIFS('Holgura'!$I$6:$I$11,'Holgura'!$B$6:$B$11,$A13,'Holgura'!$E$6:$E$11,"Víctor")+SUMIFS('Holgura'!$I$6:$I$11,'Holgura'!$B$6:$B$11,$A13,'Holgura'!$E$6:$E$11,"Ambos")+SUMIFS('Entrega'!$I$6:$I$9,'Entrega'!$B$6:$B$9,$A13,'Entrega'!$E$6:$E$9,"Víctor")+SUMIFS('Entrega'!$I$6:$I$9,'Entrega'!$B$6:$B$9,$A13,'Entrega'!$E$6:$E$9,"Ambos")+SUMIFS('Defensa'!$I$6:$I$10,'Defensa'!$B$6:$B$10,$A13,'Defensa'!$E$6:$E$10,"Víctor")+SUMIFS('Defensa'!$I$6:$I$10,'Defensa'!$B$6:$B$10,$A13,'Defensa'!$E$6:$E$10,"Ambos")</f>
         <v/>
       </c>
       <c r="E13" s="21">
-        <f>SUMIFS('S1'!$I$6:$I$32,'S1'!$B$6:$B$32,$A13,'S1'!$E$6:$E$32,"Diego")+SUMIFS('S1'!$I$6:$I$32,'S1'!$B$6:$B$32,$A13,'S1'!$E$6:$E$32,"Ambos")+SUMIFS('S2'!$I$6:$I$23,'S2'!$B$6:$B$23,$A13,'S2'!$E$6:$E$23,"Diego")+SUMIFS('S2'!$I$6:$I$23,'S2'!$B$6:$B$23,$A13,'S2'!$E$6:$E$23,"Ambos")+SUMIFS('S3'!$I$6:$I$19,'S3'!$B$6:$B$19,$A13,'S3'!$E$6:$E$19,"Diego")+SUMIFS('S3'!$I$6:$I$19,'S3'!$B$6:$B$19,$A13,'S3'!$E$6:$E$19,"Ambos")+SUMIFS('S4'!$I$6:$I$20,'S4'!$B$6:$B$20,$A13,'S4'!$E$6:$E$20,"Diego")+SUMIFS('S4'!$I$6:$I$20,'S4'!$B$6:$B$20,$A13,'S4'!$E$6:$E$20,"Ambos")+SUMIFS('S5'!$I$6:$I$20,'S5'!$B$6:$B$20,$A13,'S5'!$E$6:$E$20,"Diego")+SUMIFS('S5'!$I$6:$I$20,'S5'!$B$6:$B$20,$A13,'S5'!$E$6:$E$20,"Ambos")+SUMIFS('S6'!$I$6:$I$17,'S6'!$B$6:$B$17,$A13,'S6'!$E$6:$E$17,"Diego")+SUMIFS('S6'!$I$6:$I$17,'S6'!$B$6:$B$17,$A13,'S6'!$E$6:$E$17,"Ambos")+SUMIFS('S7'!$I$6:$I$19,'S7'!$B$6:$B$19,$A13,'S7'!$E$6:$E$19,"Diego")+SUMIFS('S7'!$I$6:$I$19,'S7'!$B$6:$B$19,$A13,'S7'!$E$6:$E$19,"Ambos")+SUMIFS('S8'!$I$6:$I$23,'S8'!$B$6:$B$23,$A13,'S8'!$E$6:$E$23,"Diego")+SUMIFS('S8'!$I$6:$I$23,'S8'!$B$6:$B$23,$A13,'S8'!$E$6:$E$23,"Ambos")+SUMIFS('S9'!$I$6:$I$15,'S9'!$B$6:$B$15,$A13,'S9'!$E$6:$E$15,"Diego")+SUMIFS('S9'!$I$6:$I$15,'S9'!$B$6:$B$15,$A13,'S9'!$E$6:$E$15,"Ambos")+SUMIFS('S10'!$I$6:$I$13,'S10'!$B$6:$B$13,$A13,'S10'!$E$6:$E$13,"Diego")+SUMIFS('S10'!$I$6:$I$13,'S10'!$B$6:$B$13,$A13,'S10'!$E$6:$E$13,"Ambos")+SUMIFS('Holgura'!$I$6:$I$11,'Holgura'!$B$6:$B$11,$A13,'Holgura'!$E$6:$E$11,"Diego")+SUMIFS('Holgura'!$I$6:$I$11,'Holgura'!$B$6:$B$11,$A13,'Holgura'!$E$6:$E$11,"Ambos")+SUMIFS('Entrega'!$I$6:$I$9,'Entrega'!$B$6:$B$9,$A13,'Entrega'!$E$6:$E$9,"Diego")+SUMIFS('Entrega'!$I$6:$I$9,'Entrega'!$B$6:$B$9,$A13,'Entrega'!$E$6:$E$9,"Ambos")+SUMIFS('Defensa'!$I$6:$I$10,'Defensa'!$B$6:$B$10,$A13,'Defensa'!$E$6:$E$10,"Diego")+SUMIFS('Defensa'!$I$6:$I$10,'Defensa'!$B$6:$B$10,$A13,'Defensa'!$E$6:$E$10,"Ambos")</f>
+        <f>SUMIFS('S1'!$I$6:$I$32,'S1'!$B$6:$B$32,$A13,'S1'!$E$6:$E$32,"Diego")+SUMIFS('S1'!$I$6:$I$32,'S1'!$B$6:$B$32,$A13,'S1'!$E$6:$E$32,"Ambos")+SUMIFS('S2'!$I$6:$I$23,'S2'!$B$6:$B$23,$A13,'S2'!$E$6:$E$23,"Diego")+SUMIFS('S2'!$I$6:$I$23,'S2'!$B$6:$B$23,$A13,'S2'!$E$6:$E$23,"Ambos")+SUMIFS('S3'!$I$6:$I$24,'S3'!$B$6:$B$24,$A13,'S3'!$E$6:$E$24,"Diego")+SUMIFS('S3'!$I$6:$I$24,'S3'!$B$6:$B$24,$A13,'S3'!$E$6:$E$24,"Ambos")+SUMIFS('S4'!$I$6:$I$22,'S4'!$B$6:$B$22,$A13,'S4'!$E$6:$E$22,"Diego")+SUMIFS('S4'!$I$6:$I$22,'S4'!$B$6:$B$22,$A13,'S4'!$E$6:$E$22,"Ambos")+SUMIFS('S5'!$I$6:$I$20,'S5'!$B$6:$B$20,$A13,'S5'!$E$6:$E$20,"Diego")+SUMIFS('S5'!$I$6:$I$20,'S5'!$B$6:$B$20,$A13,'S5'!$E$6:$E$20,"Ambos")+SUMIFS('S6'!$I$6:$I$17,'S6'!$B$6:$B$17,$A13,'S6'!$E$6:$E$17,"Diego")+SUMIFS('S6'!$I$6:$I$17,'S6'!$B$6:$B$17,$A13,'S6'!$E$6:$E$17,"Ambos")+SUMIFS('S7'!$I$6:$I$19,'S7'!$B$6:$B$19,$A13,'S7'!$E$6:$E$19,"Diego")+SUMIFS('S7'!$I$6:$I$19,'S7'!$B$6:$B$19,$A13,'S7'!$E$6:$E$19,"Ambos")+SUMIFS('S8'!$I$6:$I$23,'S8'!$B$6:$B$23,$A13,'S8'!$E$6:$E$23,"Diego")+SUMIFS('S8'!$I$6:$I$23,'S8'!$B$6:$B$23,$A13,'S8'!$E$6:$E$23,"Ambos")+SUMIFS('S9'!$I$6:$I$15,'S9'!$B$6:$B$15,$A13,'S9'!$E$6:$E$15,"Diego")+SUMIFS('S9'!$I$6:$I$15,'S9'!$B$6:$B$15,$A13,'S9'!$E$6:$E$15,"Ambos")+SUMIFS('S10'!$I$6:$I$13,'S10'!$B$6:$B$13,$A13,'S10'!$E$6:$E$13,"Diego")+SUMIFS('S10'!$I$6:$I$13,'S10'!$B$6:$B$13,$A13,'S10'!$E$6:$E$13,"Ambos")+SUMIFS('Holgura'!$I$6:$I$11,'Holgura'!$B$6:$B$11,$A13,'Holgura'!$E$6:$E$11,"Diego")+SUMIFS('Holgura'!$I$6:$I$11,'Holgura'!$B$6:$B$11,$A13,'Holgura'!$E$6:$E$11,"Ambos")+SUMIFS('Entrega'!$I$6:$I$9,'Entrega'!$B$6:$B$9,$A13,'Entrega'!$E$6:$E$9,"Diego")+SUMIFS('Entrega'!$I$6:$I$9,'Entrega'!$B$6:$B$9,$A13,'Entrega'!$E$6:$E$9,"Ambos")+SUMIFS('Defensa'!$I$6:$I$10,'Defensa'!$B$6:$B$10,$A13,'Defensa'!$E$6:$E$10,"Diego")+SUMIFS('Defensa'!$I$6:$I$10,'Defensa'!$B$6:$B$10,$A13,'Defensa'!$E$6:$E$10,"Ambos")</f>
         <v/>
       </c>
       <c r="F13" s="21">
-        <f>COUNTIFS('S1'!$B$6:$B$32,$A13,'S1'!$E$6:$E$32,"Víctor")+COUNTIFS('S1'!$B$6:$B$32,$A13,'S1'!$E$6:$E$32,"Ambos")+COUNTIFS('S2'!$B$6:$B$23,$A13,'S2'!$E$6:$E$23,"Víctor")+COUNTIFS('S2'!$B$6:$B$23,$A13,'S2'!$E$6:$E$23,"Ambos")+COUNTIFS('S3'!$B$6:$B$19,$A13,'S3'!$E$6:$E$19,"Víctor")+COUNTIFS('S3'!$B$6:$B$19,$A13,'S3'!$E$6:$E$19,"Ambos")+COUNTIFS('S4'!$B$6:$B$20,$A13,'S4'!$E$6:$E$20,"Víctor")+COUNTIFS('S4'!$B$6:$B$20,$A13,'S4'!$E$6:$E$20,"Ambos")+COUNTIFS('S5'!$B$6:$B$20,$A13,'S5'!$E$6:$E$20,"Víctor")+COUNTIFS('S5'!$B$6:$B$20,$A13,'S5'!$E$6:$E$20,"Ambos")+COUNTIFS('S6'!$B$6:$B$17,$A13,'S6'!$E$6:$E$17,"Víctor")+COUNTIFS('S6'!$B$6:$B$17,$A13,'S6'!$E$6:$E$17,"Ambos")+COUNTIFS('S7'!$B$6:$B$19,$A13,'S7'!$E$6:$E$19,"Víctor")+COUNTIFS('S7'!$B$6:$B$19,$A13,'S7'!$E$6:$E$19,"Ambos")+COUNTIFS('S8'!$B$6:$B$23,$A13,'S8'!$E$6:$E$23,"Víctor")+COUNTIFS('S8'!$B$6:$B$23,$A13,'S8'!$E$6:$E$23,"Ambos")+COUNTIFS('S9'!$B$6:$B$15,$A13,'S9'!$E$6:$E$15,"Víctor")+COUNTIFS('S9'!$B$6:$B$15,$A13,'S9'!$E$6:$E$15,"Ambos")+COUNTIFS('S10'!$B$6:$B$13,$A13,'S10'!$E$6:$E$13,"Víctor")+COUNTIFS('S10'!$B$6:$B$13,$A13,'S10'!$E$6:$E$13,"Ambos")+COUNTIFS('Holgura'!$B$6:$B$11,$A13,'Holgura'!$E$6:$E$11,"Víctor")+COUNTIFS('Holgura'!$B$6:$B$11,$A13,'Holgura'!$E$6:$E$11,"Ambos")+COUNTIFS('Entrega'!$B$6:$B$9,$A13,'Entrega'!$E$6:$E$9,"Víctor")+COUNTIFS('Entrega'!$B$6:$B$9,$A13,'Entrega'!$E$6:$E$9,"Ambos")+COUNTIFS('Defensa'!$B$6:$B$10,$A13,'Defensa'!$E$6:$E$10,"Víctor")+COUNTIFS('Defensa'!$B$6:$B$10,$A13,'Defensa'!$E$6:$E$10,"Ambos")</f>
+        <f>COUNTIFS('S1'!$B$6:$B$32,$A13,'S1'!$E$6:$E$32,"Víctor")+COUNTIFS('S1'!$B$6:$B$32,$A13,'S1'!$E$6:$E$32,"Ambos")+COUNTIFS('S2'!$B$6:$B$23,$A13,'S2'!$E$6:$E$23,"Víctor")+COUNTIFS('S2'!$B$6:$B$23,$A13,'S2'!$E$6:$E$23,"Ambos")+COUNTIFS('S3'!$B$6:$B$24,$A13,'S3'!$E$6:$E$24,"Víctor")+COUNTIFS('S3'!$B$6:$B$24,$A13,'S3'!$E$6:$E$24,"Ambos")+COUNTIFS('S4'!$B$6:$B$22,$A13,'S4'!$E$6:$E$22,"Víctor")+COUNTIFS('S4'!$B$6:$B$22,$A13,'S4'!$E$6:$E$22,"Ambos")+COUNTIFS('S5'!$B$6:$B$20,$A13,'S5'!$E$6:$E$20,"Víctor")+COUNTIFS('S5'!$B$6:$B$20,$A13,'S5'!$E$6:$E$20,"Ambos")+COUNTIFS('S6'!$B$6:$B$17,$A13,'S6'!$E$6:$E$17,"Víctor")+COUNTIFS('S6'!$B$6:$B$17,$A13,'S6'!$E$6:$E$17,"Ambos")+COUNTIFS('S7'!$B$6:$B$19,$A13,'S7'!$E$6:$E$19,"Víctor")+COUNTIFS('S7'!$B$6:$B$19,$A13,'S7'!$E$6:$E$19,"Ambos")+COUNTIFS('S8'!$B$6:$B$23,$A13,'S8'!$E$6:$E$23,"Víctor")+COUNTIFS('S8'!$B$6:$B$23,$A13,'S8'!$E$6:$E$23,"Ambos")+COUNTIFS('S9'!$B$6:$B$15,$A13,'S9'!$E$6:$E$15,"Víctor")+COUNTIFS('S9'!$B$6:$B$15,$A13,'S9'!$E$6:$E$15,"Ambos")+COUNTIFS('S10'!$B$6:$B$13,$A13,'S10'!$E$6:$E$13,"Víctor")+COUNTIFS('S10'!$B$6:$B$13,$A13,'S10'!$E$6:$E$13,"Ambos")+COUNTIFS('Holgura'!$B$6:$B$11,$A13,'Holgura'!$E$6:$E$11,"Víctor")+COUNTIFS('Holgura'!$B$6:$B$11,$A13,'Holgura'!$E$6:$E$11,"Ambos")+COUNTIFS('Entrega'!$B$6:$B$9,$A13,'Entrega'!$E$6:$E$9,"Víctor")+COUNTIFS('Entrega'!$B$6:$B$9,$A13,'Entrega'!$E$6:$E$9,"Ambos")+COUNTIFS('Defensa'!$B$6:$B$10,$A13,'Defensa'!$E$6:$E$10,"Víctor")+COUNTIFS('Defensa'!$B$6:$B$10,$A13,'Defensa'!$E$6:$E$10,"Ambos")</f>
         <v/>
       </c>
       <c r="G13" s="21">
-        <f>COUNTIFS('S1'!$B$6:$B$32,$A13,'S1'!$E$6:$E$32,"Diego")+COUNTIFS('S1'!$B$6:$B$32,$A13,'S1'!$E$6:$E$32,"Ambos")+COUNTIFS('S2'!$B$6:$B$23,$A13,'S2'!$E$6:$E$23,"Diego")+COUNTIFS('S2'!$B$6:$B$23,$A13,'S2'!$E$6:$E$23,"Ambos")+COUNTIFS('S3'!$B$6:$B$19,$A13,'S3'!$E$6:$E$19,"Diego")+COUNTIFS('S3'!$B$6:$B$19,$A13,'S3'!$E$6:$E$19,"Ambos")+COUNTIFS('S4'!$B$6:$B$20,$A13,'S4'!$E$6:$E$20,"Diego")+COUNTIFS('S4'!$B$6:$B$20,$A13,'S4'!$E$6:$E$20,"Ambos")+COUNTIFS('S5'!$B$6:$B$20,$A13,'S5'!$E$6:$E$20,"Diego")+COUNTIFS('S5'!$B$6:$B$20,$A13,'S5'!$E$6:$E$20,"Ambos")+COUNTIFS('S6'!$B$6:$B$17,$A13,'S6'!$E$6:$E$17,"Diego")+COUNTIFS('S6'!$B$6:$B$17,$A13,'S6'!$E$6:$E$17,"Ambos")+COUNTIFS('S7'!$B$6:$B$19,$A13,'S7'!$E$6:$E$19,"Diego")+COUNTIFS('S7'!$B$6:$B$19,$A13,'S7'!$E$6:$E$19,"Ambos")+COUNTIFS('S8'!$B$6:$B$23,$A13,'S8'!$E$6:$E$23,"Diego")+COUNTIFS('S8'!$B$6:$B$23,$A13,'S8'!$E$6:$E$23,"Ambos")+COUNTIFS('S9'!$B$6:$B$15,$A13,'S9'!$E$6:$E$15,"Diego")+COUNTIFS('S9'!$B$6:$B$15,$A13,'S9'!$E$6:$E$15,"Ambos")+COUNTIFS('S10'!$B$6:$B$13,$A13,'S10'!$E$6:$E$13,"Diego")+COUNTIFS('S10'!$B$6:$B$13,$A13,'S10'!$E$6:$E$13,"Ambos")+COUNTIFS('Holgura'!$B$6:$B$11,$A13,'Holgura'!$E$6:$E$11,"Diego")+COUNTIFS('Holgura'!$B$6:$B$11,$A13,'Holgura'!$E$6:$E$11,"Ambos")+COUNTIFS('Entrega'!$B$6:$B$9,$A13,'Entrega'!$E$6:$E$9,"Diego")+COUNTIFS('Entrega'!$B$6:$B$9,$A13,'Entrega'!$E$6:$E$9,"Ambos")+COUNTIFS('Defensa'!$B$6:$B$10,$A13,'Defensa'!$E$6:$E$10,"Diego")+COUNTIFS('Defensa'!$B$6:$B$10,$A13,'Defensa'!$E$6:$E$10,"Ambos")</f>
+        <f>COUNTIFS('S1'!$B$6:$B$32,$A13,'S1'!$E$6:$E$32,"Diego")+COUNTIFS('S1'!$B$6:$B$32,$A13,'S1'!$E$6:$E$32,"Ambos")+COUNTIFS('S2'!$B$6:$B$23,$A13,'S2'!$E$6:$E$23,"Diego")+COUNTIFS('S2'!$B$6:$B$23,$A13,'S2'!$E$6:$E$23,"Ambos")+COUNTIFS('S3'!$B$6:$B$24,$A13,'S3'!$E$6:$E$24,"Diego")+COUNTIFS('S3'!$B$6:$B$24,$A13,'S3'!$E$6:$E$24,"Ambos")+COUNTIFS('S4'!$B$6:$B$22,$A13,'S4'!$E$6:$E$22,"Diego")+COUNTIFS('S4'!$B$6:$B$22,$A13,'S4'!$E$6:$E$22,"Ambos")+COUNTIFS('S5'!$B$6:$B$20,$A13,'S5'!$E$6:$E$20,"Diego")+COUNTIFS('S5'!$B$6:$B$20,$A13,'S5'!$E$6:$E$20,"Ambos")+COUNTIFS('S6'!$B$6:$B$17,$A13,'S6'!$E$6:$E$17,"Diego")+COUNTIFS('S6'!$B$6:$B$17,$A13,'S6'!$E$6:$E$17,"Ambos")+COUNTIFS('S7'!$B$6:$B$19,$A13,'S7'!$E$6:$E$19,"Diego")+COUNTIFS('S7'!$B$6:$B$19,$A13,'S7'!$E$6:$E$19,"Ambos")+COUNTIFS('S8'!$B$6:$B$23,$A13,'S8'!$E$6:$E$23,"Diego")+COUNTIFS('S8'!$B$6:$B$23,$A13,'S8'!$E$6:$E$23,"Ambos")+COUNTIFS('S9'!$B$6:$B$15,$A13,'S9'!$E$6:$E$15,"Diego")+COUNTIFS('S9'!$B$6:$B$15,$A13,'S9'!$E$6:$E$15,"Ambos")+COUNTIFS('S10'!$B$6:$B$13,$A13,'S10'!$E$6:$E$13,"Diego")+COUNTIFS('S10'!$B$6:$B$13,$A13,'S10'!$E$6:$E$13,"Ambos")+COUNTIFS('Holgura'!$B$6:$B$11,$A13,'Holgura'!$E$6:$E$11,"Diego")+COUNTIFS('Holgura'!$B$6:$B$11,$A13,'Holgura'!$E$6:$E$11,"Ambos")+COUNTIFS('Entrega'!$B$6:$B$9,$A13,'Entrega'!$E$6:$E$9,"Diego")+COUNTIFS('Entrega'!$B$6:$B$9,$A13,'Entrega'!$E$6:$E$9,"Ambos")+COUNTIFS('Defensa'!$B$6:$B$10,$A13,'Defensa'!$E$6:$E$10,"Diego")+COUNTIFS('Defensa'!$B$6:$B$10,$A13,'Defensa'!$E$6:$E$10,"Ambos")</f>
         <v/>
       </c>
     </row>
@@ -8941,19 +8962,19 @@
         <v/>
       </c>
       <c r="D14" s="21">
-        <f>SUMIFS('S1'!$I$6:$I$32,'S1'!$B$6:$B$32,$A14,'S1'!$E$6:$E$32,"Víctor")+SUMIFS('S1'!$I$6:$I$32,'S1'!$B$6:$B$32,$A14,'S1'!$E$6:$E$32,"Ambos")+SUMIFS('S2'!$I$6:$I$23,'S2'!$B$6:$B$23,$A14,'S2'!$E$6:$E$23,"Víctor")+SUMIFS('S2'!$I$6:$I$23,'S2'!$B$6:$B$23,$A14,'S2'!$E$6:$E$23,"Ambos")+SUMIFS('S3'!$I$6:$I$19,'S3'!$B$6:$B$19,$A14,'S3'!$E$6:$E$19,"Víctor")+SUMIFS('S3'!$I$6:$I$19,'S3'!$B$6:$B$19,$A14,'S3'!$E$6:$E$19,"Ambos")+SUMIFS('S4'!$I$6:$I$20,'S4'!$B$6:$B$20,$A14,'S4'!$E$6:$E$20,"Víctor")+SUMIFS('S4'!$I$6:$I$20,'S4'!$B$6:$B$20,$A14,'S4'!$E$6:$E$20,"Ambos")+SUMIFS('S5'!$I$6:$I$20,'S5'!$B$6:$B$20,$A14,'S5'!$E$6:$E$20,"Víctor")+SUMIFS('S5'!$I$6:$I$20,'S5'!$B$6:$B$20,$A14,'S5'!$E$6:$E$20,"Ambos")+SUMIFS('S6'!$I$6:$I$17,'S6'!$B$6:$B$17,$A14,'S6'!$E$6:$E$17,"Víctor")+SUMIFS('S6'!$I$6:$I$17,'S6'!$B$6:$B$17,$A14,'S6'!$E$6:$E$17,"Ambos")+SUMIFS('S7'!$I$6:$I$19,'S7'!$B$6:$B$19,$A14,'S7'!$E$6:$E$19,"Víctor")+SUMIFS('S7'!$I$6:$I$19,'S7'!$B$6:$B$19,$A14,'S7'!$E$6:$E$19,"Ambos")+SUMIFS('S8'!$I$6:$I$23,'S8'!$B$6:$B$23,$A14,'S8'!$E$6:$E$23,"Víctor")+SUMIFS('S8'!$I$6:$I$23,'S8'!$B$6:$B$23,$A14,'S8'!$E$6:$E$23,"Ambos")+SUMIFS('S9'!$I$6:$I$15,'S9'!$B$6:$B$15,$A14,'S9'!$E$6:$E$15,"Víctor")+SUMIFS('S9'!$I$6:$I$15,'S9'!$B$6:$B$15,$A14,'S9'!$E$6:$E$15,"Ambos")+SUMIFS('S10'!$I$6:$I$13,'S10'!$B$6:$B$13,$A14,'S10'!$E$6:$E$13,"Víctor")+SUMIFS('S10'!$I$6:$I$13,'S10'!$B$6:$B$13,$A14,'S10'!$E$6:$E$13,"Ambos")+SUMIFS('Holgura'!$I$6:$I$11,'Holgura'!$B$6:$B$11,$A14,'Holgura'!$E$6:$E$11,"Víctor")+SUMIFS('Holgura'!$I$6:$I$11,'Holgura'!$B$6:$B$11,$A14,'Holgura'!$E$6:$E$11,"Ambos")+SUMIFS('Entrega'!$I$6:$I$9,'Entrega'!$B$6:$B$9,$A14,'Entrega'!$E$6:$E$9,"Víctor")+SUMIFS('Entrega'!$I$6:$I$9,'Entrega'!$B$6:$B$9,$A14,'Entrega'!$E$6:$E$9,"Ambos")+SUMIFS('Defensa'!$I$6:$I$10,'Defensa'!$B$6:$B$10,$A14,'Defensa'!$E$6:$E$10,"Víctor")+SUMIFS('Defensa'!$I$6:$I$10,'Defensa'!$B$6:$B$10,$A14,'Defensa'!$E$6:$E$10,"Ambos")</f>
+        <f>SUMIFS('S1'!$I$6:$I$32,'S1'!$B$6:$B$32,$A14,'S1'!$E$6:$E$32,"Víctor")+SUMIFS('S1'!$I$6:$I$32,'S1'!$B$6:$B$32,$A14,'S1'!$E$6:$E$32,"Ambos")+SUMIFS('S2'!$I$6:$I$23,'S2'!$B$6:$B$23,$A14,'S2'!$E$6:$E$23,"Víctor")+SUMIFS('S2'!$I$6:$I$23,'S2'!$B$6:$B$23,$A14,'S2'!$E$6:$E$23,"Ambos")+SUMIFS('S3'!$I$6:$I$24,'S3'!$B$6:$B$24,$A14,'S3'!$E$6:$E$24,"Víctor")+SUMIFS('S3'!$I$6:$I$24,'S3'!$B$6:$B$24,$A14,'S3'!$E$6:$E$24,"Ambos")+SUMIFS('S4'!$I$6:$I$22,'S4'!$B$6:$B$22,$A14,'S4'!$E$6:$E$22,"Víctor")+SUMIFS('S4'!$I$6:$I$22,'S4'!$B$6:$B$22,$A14,'S4'!$E$6:$E$22,"Ambos")+SUMIFS('S5'!$I$6:$I$20,'S5'!$B$6:$B$20,$A14,'S5'!$E$6:$E$20,"Víctor")+SUMIFS('S5'!$I$6:$I$20,'S5'!$B$6:$B$20,$A14,'S5'!$E$6:$E$20,"Ambos")+SUMIFS('S6'!$I$6:$I$17,'S6'!$B$6:$B$17,$A14,'S6'!$E$6:$E$17,"Víctor")+SUMIFS('S6'!$I$6:$I$17,'S6'!$B$6:$B$17,$A14,'S6'!$E$6:$E$17,"Ambos")+SUMIFS('S7'!$I$6:$I$19,'S7'!$B$6:$B$19,$A14,'S7'!$E$6:$E$19,"Víctor")+SUMIFS('S7'!$I$6:$I$19,'S7'!$B$6:$B$19,$A14,'S7'!$E$6:$E$19,"Ambos")+SUMIFS('S8'!$I$6:$I$23,'S8'!$B$6:$B$23,$A14,'S8'!$E$6:$E$23,"Víctor")+SUMIFS('S8'!$I$6:$I$23,'S8'!$B$6:$B$23,$A14,'S8'!$E$6:$E$23,"Ambos")+SUMIFS('S9'!$I$6:$I$15,'S9'!$B$6:$B$15,$A14,'S9'!$E$6:$E$15,"Víctor")+SUMIFS('S9'!$I$6:$I$15,'S9'!$B$6:$B$15,$A14,'S9'!$E$6:$E$15,"Ambos")+SUMIFS('S10'!$I$6:$I$13,'S10'!$B$6:$B$13,$A14,'S10'!$E$6:$E$13,"Víctor")+SUMIFS('S10'!$I$6:$I$13,'S10'!$B$6:$B$13,$A14,'S10'!$E$6:$E$13,"Ambos")+SUMIFS('Holgura'!$I$6:$I$11,'Holgura'!$B$6:$B$11,$A14,'Holgura'!$E$6:$E$11,"Víctor")+SUMIFS('Holgura'!$I$6:$I$11,'Holgura'!$B$6:$B$11,$A14,'Holgura'!$E$6:$E$11,"Ambos")+SUMIFS('Entrega'!$I$6:$I$9,'Entrega'!$B$6:$B$9,$A14,'Entrega'!$E$6:$E$9,"Víctor")+SUMIFS('Entrega'!$I$6:$I$9,'Entrega'!$B$6:$B$9,$A14,'Entrega'!$E$6:$E$9,"Ambos")+SUMIFS('Defensa'!$I$6:$I$10,'Defensa'!$B$6:$B$10,$A14,'Defensa'!$E$6:$E$10,"Víctor")+SUMIFS('Defensa'!$I$6:$I$10,'Defensa'!$B$6:$B$10,$A14,'Defensa'!$E$6:$E$10,"Ambos")</f>
         <v/>
       </c>
       <c r="E14" s="21">
-        <f>SUMIFS('S1'!$I$6:$I$32,'S1'!$B$6:$B$32,$A14,'S1'!$E$6:$E$32,"Diego")+SUMIFS('S1'!$I$6:$I$32,'S1'!$B$6:$B$32,$A14,'S1'!$E$6:$E$32,"Ambos")+SUMIFS('S2'!$I$6:$I$23,'S2'!$B$6:$B$23,$A14,'S2'!$E$6:$E$23,"Diego")+SUMIFS('S2'!$I$6:$I$23,'S2'!$B$6:$B$23,$A14,'S2'!$E$6:$E$23,"Ambos")+SUMIFS('S3'!$I$6:$I$19,'S3'!$B$6:$B$19,$A14,'S3'!$E$6:$E$19,"Diego")+SUMIFS('S3'!$I$6:$I$19,'S3'!$B$6:$B$19,$A14,'S3'!$E$6:$E$19,"Ambos")+SUMIFS('S4'!$I$6:$I$20,'S4'!$B$6:$B$20,$A14,'S4'!$E$6:$E$20,"Diego")+SUMIFS('S4'!$I$6:$I$20,'S4'!$B$6:$B$20,$A14,'S4'!$E$6:$E$20,"Ambos")+SUMIFS('S5'!$I$6:$I$20,'S5'!$B$6:$B$20,$A14,'S5'!$E$6:$E$20,"Diego")+SUMIFS('S5'!$I$6:$I$20,'S5'!$B$6:$B$20,$A14,'S5'!$E$6:$E$20,"Ambos")+SUMIFS('S6'!$I$6:$I$17,'S6'!$B$6:$B$17,$A14,'S6'!$E$6:$E$17,"Diego")+SUMIFS('S6'!$I$6:$I$17,'S6'!$B$6:$B$17,$A14,'S6'!$E$6:$E$17,"Ambos")+SUMIFS('S7'!$I$6:$I$19,'S7'!$B$6:$B$19,$A14,'S7'!$E$6:$E$19,"Diego")+SUMIFS('S7'!$I$6:$I$19,'S7'!$B$6:$B$19,$A14,'S7'!$E$6:$E$19,"Ambos")+SUMIFS('S8'!$I$6:$I$23,'S8'!$B$6:$B$23,$A14,'S8'!$E$6:$E$23,"Diego")+SUMIFS('S8'!$I$6:$I$23,'S8'!$B$6:$B$23,$A14,'S8'!$E$6:$E$23,"Ambos")+SUMIFS('S9'!$I$6:$I$15,'S9'!$B$6:$B$15,$A14,'S9'!$E$6:$E$15,"Diego")+SUMIFS('S9'!$I$6:$I$15,'S9'!$B$6:$B$15,$A14,'S9'!$E$6:$E$15,"Ambos")+SUMIFS('S10'!$I$6:$I$13,'S10'!$B$6:$B$13,$A14,'S10'!$E$6:$E$13,"Diego")+SUMIFS('S10'!$I$6:$I$13,'S10'!$B$6:$B$13,$A14,'S10'!$E$6:$E$13,"Ambos")+SUMIFS('Holgura'!$I$6:$I$11,'Holgura'!$B$6:$B$11,$A14,'Holgura'!$E$6:$E$11,"Diego")+SUMIFS('Holgura'!$I$6:$I$11,'Holgura'!$B$6:$B$11,$A14,'Holgura'!$E$6:$E$11,"Ambos")+SUMIFS('Entrega'!$I$6:$I$9,'Entrega'!$B$6:$B$9,$A14,'Entrega'!$E$6:$E$9,"Diego")+SUMIFS('Entrega'!$I$6:$I$9,'Entrega'!$B$6:$B$9,$A14,'Entrega'!$E$6:$E$9,"Ambos")+SUMIFS('Defensa'!$I$6:$I$10,'Defensa'!$B$6:$B$10,$A14,'Defensa'!$E$6:$E$10,"Diego")+SUMIFS('Defensa'!$I$6:$I$10,'Defensa'!$B$6:$B$10,$A14,'Defensa'!$E$6:$E$10,"Ambos")</f>
+        <f>SUMIFS('S1'!$I$6:$I$32,'S1'!$B$6:$B$32,$A14,'S1'!$E$6:$E$32,"Diego")+SUMIFS('S1'!$I$6:$I$32,'S1'!$B$6:$B$32,$A14,'S1'!$E$6:$E$32,"Ambos")+SUMIFS('S2'!$I$6:$I$23,'S2'!$B$6:$B$23,$A14,'S2'!$E$6:$E$23,"Diego")+SUMIFS('S2'!$I$6:$I$23,'S2'!$B$6:$B$23,$A14,'S2'!$E$6:$E$23,"Ambos")+SUMIFS('S3'!$I$6:$I$24,'S3'!$B$6:$B$24,$A14,'S3'!$E$6:$E$24,"Diego")+SUMIFS('S3'!$I$6:$I$24,'S3'!$B$6:$B$24,$A14,'S3'!$E$6:$E$24,"Ambos")+SUMIFS('S4'!$I$6:$I$22,'S4'!$B$6:$B$22,$A14,'S4'!$E$6:$E$22,"Diego")+SUMIFS('S4'!$I$6:$I$22,'S4'!$B$6:$B$22,$A14,'S4'!$E$6:$E$22,"Ambos")+SUMIFS('S5'!$I$6:$I$20,'S5'!$B$6:$B$20,$A14,'S5'!$E$6:$E$20,"Diego")+SUMIFS('S5'!$I$6:$I$20,'S5'!$B$6:$B$20,$A14,'S5'!$E$6:$E$20,"Ambos")+SUMIFS('S6'!$I$6:$I$17,'S6'!$B$6:$B$17,$A14,'S6'!$E$6:$E$17,"Diego")+SUMIFS('S6'!$I$6:$I$17,'S6'!$B$6:$B$17,$A14,'S6'!$E$6:$E$17,"Ambos")+SUMIFS('S7'!$I$6:$I$19,'S7'!$B$6:$B$19,$A14,'S7'!$E$6:$E$19,"Diego")+SUMIFS('S7'!$I$6:$I$19,'S7'!$B$6:$B$19,$A14,'S7'!$E$6:$E$19,"Ambos")+SUMIFS('S8'!$I$6:$I$23,'S8'!$B$6:$B$23,$A14,'S8'!$E$6:$E$23,"Diego")+SUMIFS('S8'!$I$6:$I$23,'S8'!$B$6:$B$23,$A14,'S8'!$E$6:$E$23,"Ambos")+SUMIFS('S9'!$I$6:$I$15,'S9'!$B$6:$B$15,$A14,'S9'!$E$6:$E$15,"Diego")+SUMIFS('S9'!$I$6:$I$15,'S9'!$B$6:$B$15,$A14,'S9'!$E$6:$E$15,"Ambos")+SUMIFS('S10'!$I$6:$I$13,'S10'!$B$6:$B$13,$A14,'S10'!$E$6:$E$13,"Diego")+SUMIFS('S10'!$I$6:$I$13,'S10'!$B$6:$B$13,$A14,'S10'!$E$6:$E$13,"Ambos")+SUMIFS('Holgura'!$I$6:$I$11,'Holgura'!$B$6:$B$11,$A14,'Holgura'!$E$6:$E$11,"Diego")+SUMIFS('Holgura'!$I$6:$I$11,'Holgura'!$B$6:$B$11,$A14,'Holgura'!$E$6:$E$11,"Ambos")+SUMIFS('Entrega'!$I$6:$I$9,'Entrega'!$B$6:$B$9,$A14,'Entrega'!$E$6:$E$9,"Diego")+SUMIFS('Entrega'!$I$6:$I$9,'Entrega'!$B$6:$B$9,$A14,'Entrega'!$E$6:$E$9,"Ambos")+SUMIFS('Defensa'!$I$6:$I$10,'Defensa'!$B$6:$B$10,$A14,'Defensa'!$E$6:$E$10,"Diego")+SUMIFS('Defensa'!$I$6:$I$10,'Defensa'!$B$6:$B$10,$A14,'Defensa'!$E$6:$E$10,"Ambos")</f>
         <v/>
       </c>
       <c r="F14" s="21">
-        <f>COUNTIFS('S1'!$B$6:$B$32,$A14,'S1'!$E$6:$E$32,"Víctor")+COUNTIFS('S1'!$B$6:$B$32,$A14,'S1'!$E$6:$E$32,"Ambos")+COUNTIFS('S2'!$B$6:$B$23,$A14,'S2'!$E$6:$E$23,"Víctor")+COUNTIFS('S2'!$B$6:$B$23,$A14,'S2'!$E$6:$E$23,"Ambos")+COUNTIFS('S3'!$B$6:$B$19,$A14,'S3'!$E$6:$E$19,"Víctor")+COUNTIFS('S3'!$B$6:$B$19,$A14,'S3'!$E$6:$E$19,"Ambos")+COUNTIFS('S4'!$B$6:$B$20,$A14,'S4'!$E$6:$E$20,"Víctor")+COUNTIFS('S4'!$B$6:$B$20,$A14,'S4'!$E$6:$E$20,"Ambos")+COUNTIFS('S5'!$B$6:$B$20,$A14,'S5'!$E$6:$E$20,"Víctor")+COUNTIFS('S5'!$B$6:$B$20,$A14,'S5'!$E$6:$E$20,"Ambos")+COUNTIFS('S6'!$B$6:$B$17,$A14,'S6'!$E$6:$E$17,"Víctor")+COUNTIFS('S6'!$B$6:$B$17,$A14,'S6'!$E$6:$E$17,"Ambos")+COUNTIFS('S7'!$B$6:$B$19,$A14,'S7'!$E$6:$E$19,"Víctor")+COUNTIFS('S7'!$B$6:$B$19,$A14,'S7'!$E$6:$E$19,"Ambos")+COUNTIFS('S8'!$B$6:$B$23,$A14,'S8'!$E$6:$E$23,"Víctor")+COUNTIFS('S8'!$B$6:$B$23,$A14,'S8'!$E$6:$E$23,"Ambos")+COUNTIFS('S9'!$B$6:$B$15,$A14,'S9'!$E$6:$E$15,"Víctor")+COUNTIFS('S9'!$B$6:$B$15,$A14,'S9'!$E$6:$E$15,"Ambos")+COUNTIFS('S10'!$B$6:$B$13,$A14,'S10'!$E$6:$E$13,"Víctor")+COUNTIFS('S10'!$B$6:$B$13,$A14,'S10'!$E$6:$E$13,"Ambos")+COUNTIFS('Holgura'!$B$6:$B$11,$A14,'Holgura'!$E$6:$E$11,"Víctor")+COUNTIFS('Holgura'!$B$6:$B$11,$A14,'Holgura'!$E$6:$E$11,"Ambos")+COUNTIFS('Entrega'!$B$6:$B$9,$A14,'Entrega'!$E$6:$E$9,"Víctor")+COUNTIFS('Entrega'!$B$6:$B$9,$A14,'Entrega'!$E$6:$E$9,"Ambos")+COUNTIFS('Defensa'!$B$6:$B$10,$A14,'Defensa'!$E$6:$E$10,"Víctor")+COUNTIFS('Defensa'!$B$6:$B$10,$A14,'Defensa'!$E$6:$E$10,"Ambos")</f>
+        <f>COUNTIFS('S1'!$B$6:$B$32,$A14,'S1'!$E$6:$E$32,"Víctor")+COUNTIFS('S1'!$B$6:$B$32,$A14,'S1'!$E$6:$E$32,"Ambos")+COUNTIFS('S2'!$B$6:$B$23,$A14,'S2'!$E$6:$E$23,"Víctor")+COUNTIFS('S2'!$B$6:$B$23,$A14,'S2'!$E$6:$E$23,"Ambos")+COUNTIFS('S3'!$B$6:$B$24,$A14,'S3'!$E$6:$E$24,"Víctor")+COUNTIFS('S3'!$B$6:$B$24,$A14,'S3'!$E$6:$E$24,"Ambos")+COUNTIFS('S4'!$B$6:$B$22,$A14,'S4'!$E$6:$E$22,"Víctor")+COUNTIFS('S4'!$B$6:$B$22,$A14,'S4'!$E$6:$E$22,"Ambos")+COUNTIFS('S5'!$B$6:$B$20,$A14,'S5'!$E$6:$E$20,"Víctor")+COUNTIFS('S5'!$B$6:$B$20,$A14,'S5'!$E$6:$E$20,"Ambos")+COUNTIFS('S6'!$B$6:$B$17,$A14,'S6'!$E$6:$E$17,"Víctor")+COUNTIFS('S6'!$B$6:$B$17,$A14,'S6'!$E$6:$E$17,"Ambos")+COUNTIFS('S7'!$B$6:$B$19,$A14,'S7'!$E$6:$E$19,"Víctor")+COUNTIFS('S7'!$B$6:$B$19,$A14,'S7'!$E$6:$E$19,"Ambos")+COUNTIFS('S8'!$B$6:$B$23,$A14,'S8'!$E$6:$E$23,"Víctor")+COUNTIFS('S8'!$B$6:$B$23,$A14,'S8'!$E$6:$E$23,"Ambos")+COUNTIFS('S9'!$B$6:$B$15,$A14,'S9'!$E$6:$E$15,"Víctor")+COUNTIFS('S9'!$B$6:$B$15,$A14,'S9'!$E$6:$E$15,"Ambos")+COUNTIFS('S10'!$B$6:$B$13,$A14,'S10'!$E$6:$E$13,"Víctor")+COUNTIFS('S10'!$B$6:$B$13,$A14,'S10'!$E$6:$E$13,"Ambos")+COUNTIFS('Holgura'!$B$6:$B$11,$A14,'Holgura'!$E$6:$E$11,"Víctor")+COUNTIFS('Holgura'!$B$6:$B$11,$A14,'Holgura'!$E$6:$E$11,"Ambos")+COUNTIFS('Entrega'!$B$6:$B$9,$A14,'Entrega'!$E$6:$E$9,"Víctor")+COUNTIFS('Entrega'!$B$6:$B$9,$A14,'Entrega'!$E$6:$E$9,"Ambos")+COUNTIFS('Defensa'!$B$6:$B$10,$A14,'Defensa'!$E$6:$E$10,"Víctor")+COUNTIFS('Defensa'!$B$6:$B$10,$A14,'Defensa'!$E$6:$E$10,"Ambos")</f>
         <v/>
       </c>
       <c r="G14" s="21">
-        <f>COUNTIFS('S1'!$B$6:$B$32,$A14,'S1'!$E$6:$E$32,"Diego")+COUNTIFS('S1'!$B$6:$B$32,$A14,'S1'!$E$6:$E$32,"Ambos")+COUNTIFS('S2'!$B$6:$B$23,$A14,'S2'!$E$6:$E$23,"Diego")+COUNTIFS('S2'!$B$6:$B$23,$A14,'S2'!$E$6:$E$23,"Ambos")+COUNTIFS('S3'!$B$6:$B$19,$A14,'S3'!$E$6:$E$19,"Diego")+COUNTIFS('S3'!$B$6:$B$19,$A14,'S3'!$E$6:$E$19,"Ambos")+COUNTIFS('S4'!$B$6:$B$20,$A14,'S4'!$E$6:$E$20,"Diego")+COUNTIFS('S4'!$B$6:$B$20,$A14,'S4'!$E$6:$E$20,"Ambos")+COUNTIFS('S5'!$B$6:$B$20,$A14,'S5'!$E$6:$E$20,"Diego")+COUNTIFS('S5'!$B$6:$B$20,$A14,'S5'!$E$6:$E$20,"Ambos")+COUNTIFS('S6'!$B$6:$B$17,$A14,'S6'!$E$6:$E$17,"Diego")+COUNTIFS('S6'!$B$6:$B$17,$A14,'S6'!$E$6:$E$17,"Ambos")+COUNTIFS('S7'!$B$6:$B$19,$A14,'S7'!$E$6:$E$19,"Diego")+COUNTIFS('S7'!$B$6:$B$19,$A14,'S7'!$E$6:$E$19,"Ambos")+COUNTIFS('S8'!$B$6:$B$23,$A14,'S8'!$E$6:$E$23,"Diego")+COUNTIFS('S8'!$B$6:$B$23,$A14,'S8'!$E$6:$E$23,"Ambos")+COUNTIFS('S9'!$B$6:$B$15,$A14,'S9'!$E$6:$E$15,"Diego")+COUNTIFS('S9'!$B$6:$B$15,$A14,'S9'!$E$6:$E$15,"Ambos")+COUNTIFS('S10'!$B$6:$B$13,$A14,'S10'!$E$6:$E$13,"Diego")+COUNTIFS('S10'!$B$6:$B$13,$A14,'S10'!$E$6:$E$13,"Ambos")+COUNTIFS('Holgura'!$B$6:$B$11,$A14,'Holgura'!$E$6:$E$11,"Diego")+COUNTIFS('Holgura'!$B$6:$B$11,$A14,'Holgura'!$E$6:$E$11,"Ambos")+COUNTIFS('Entrega'!$B$6:$B$9,$A14,'Entrega'!$E$6:$E$9,"Diego")+COUNTIFS('Entrega'!$B$6:$B$9,$A14,'Entrega'!$E$6:$E$9,"Ambos")+COUNTIFS('Defensa'!$B$6:$B$10,$A14,'Defensa'!$E$6:$E$10,"Diego")+COUNTIFS('Defensa'!$B$6:$B$10,$A14,'Defensa'!$E$6:$E$10,"Ambos")</f>
+        <f>COUNTIFS('S1'!$B$6:$B$32,$A14,'S1'!$E$6:$E$32,"Diego")+COUNTIFS('S1'!$B$6:$B$32,$A14,'S1'!$E$6:$E$32,"Ambos")+COUNTIFS('S2'!$B$6:$B$23,$A14,'S2'!$E$6:$E$23,"Diego")+COUNTIFS('S2'!$B$6:$B$23,$A14,'S2'!$E$6:$E$23,"Ambos")+COUNTIFS('S3'!$B$6:$B$24,$A14,'S3'!$E$6:$E$24,"Diego")+COUNTIFS('S3'!$B$6:$B$24,$A14,'S3'!$E$6:$E$24,"Ambos")+COUNTIFS('S4'!$B$6:$B$22,$A14,'S4'!$E$6:$E$22,"Diego")+COUNTIFS('S4'!$B$6:$B$22,$A14,'S4'!$E$6:$E$22,"Ambos")+COUNTIFS('S5'!$B$6:$B$20,$A14,'S5'!$E$6:$E$20,"Diego")+COUNTIFS('S5'!$B$6:$B$20,$A14,'S5'!$E$6:$E$20,"Ambos")+COUNTIFS('S6'!$B$6:$B$17,$A14,'S6'!$E$6:$E$17,"Diego")+COUNTIFS('S6'!$B$6:$B$17,$A14,'S6'!$E$6:$E$17,"Ambos")+COUNTIFS('S7'!$B$6:$B$19,$A14,'S7'!$E$6:$E$19,"Diego")+COUNTIFS('S7'!$B$6:$B$19,$A14,'S7'!$E$6:$E$19,"Ambos")+COUNTIFS('S8'!$B$6:$B$23,$A14,'S8'!$E$6:$E$23,"Diego")+COUNTIFS('S8'!$B$6:$B$23,$A14,'S8'!$E$6:$E$23,"Ambos")+COUNTIFS('S9'!$B$6:$B$15,$A14,'S9'!$E$6:$E$15,"Diego")+COUNTIFS('S9'!$B$6:$B$15,$A14,'S9'!$E$6:$E$15,"Ambos")+COUNTIFS('S10'!$B$6:$B$13,$A14,'S10'!$E$6:$E$13,"Diego")+COUNTIFS('S10'!$B$6:$B$13,$A14,'S10'!$E$6:$E$13,"Ambos")+COUNTIFS('Holgura'!$B$6:$B$11,$A14,'Holgura'!$E$6:$E$11,"Diego")+COUNTIFS('Holgura'!$B$6:$B$11,$A14,'Holgura'!$E$6:$E$11,"Ambos")+COUNTIFS('Entrega'!$B$6:$B$9,$A14,'Entrega'!$E$6:$E$9,"Diego")+COUNTIFS('Entrega'!$B$6:$B$9,$A14,'Entrega'!$E$6:$E$9,"Ambos")+COUNTIFS('Defensa'!$B$6:$B$10,$A14,'Defensa'!$E$6:$E$10,"Diego")+COUNTIFS('Defensa'!$B$6:$B$10,$A14,'Defensa'!$E$6:$E$10,"Ambos")</f>
         <v/>
       </c>
     </row>
@@ -8970,19 +8991,19 @@
         <v/>
       </c>
       <c r="D15" s="21">
-        <f>SUMIFS('S1'!$I$6:$I$32,'S1'!$B$6:$B$32,$A15,'S1'!$E$6:$E$32,"Víctor")+SUMIFS('S1'!$I$6:$I$32,'S1'!$B$6:$B$32,$A15,'S1'!$E$6:$E$32,"Ambos")+SUMIFS('S2'!$I$6:$I$23,'S2'!$B$6:$B$23,$A15,'S2'!$E$6:$E$23,"Víctor")+SUMIFS('S2'!$I$6:$I$23,'S2'!$B$6:$B$23,$A15,'S2'!$E$6:$E$23,"Ambos")+SUMIFS('S3'!$I$6:$I$19,'S3'!$B$6:$B$19,$A15,'S3'!$E$6:$E$19,"Víctor")+SUMIFS('S3'!$I$6:$I$19,'S3'!$B$6:$B$19,$A15,'S3'!$E$6:$E$19,"Ambos")+SUMIFS('S4'!$I$6:$I$20,'S4'!$B$6:$B$20,$A15,'S4'!$E$6:$E$20,"Víctor")+SUMIFS('S4'!$I$6:$I$20,'S4'!$B$6:$B$20,$A15,'S4'!$E$6:$E$20,"Ambos")+SUMIFS('S5'!$I$6:$I$20,'S5'!$B$6:$B$20,$A15,'S5'!$E$6:$E$20,"Víctor")+SUMIFS('S5'!$I$6:$I$20,'S5'!$B$6:$B$20,$A15,'S5'!$E$6:$E$20,"Ambos")+SUMIFS('S6'!$I$6:$I$17,'S6'!$B$6:$B$17,$A15,'S6'!$E$6:$E$17,"Víctor")+SUMIFS('S6'!$I$6:$I$17,'S6'!$B$6:$B$17,$A15,'S6'!$E$6:$E$17,"Ambos")+SUMIFS('S7'!$I$6:$I$19,'S7'!$B$6:$B$19,$A15,'S7'!$E$6:$E$19,"Víctor")+SUMIFS('S7'!$I$6:$I$19,'S7'!$B$6:$B$19,$A15,'S7'!$E$6:$E$19,"Ambos")+SUMIFS('S8'!$I$6:$I$23,'S8'!$B$6:$B$23,$A15,'S8'!$E$6:$E$23,"Víctor")+SUMIFS('S8'!$I$6:$I$23,'S8'!$B$6:$B$23,$A15,'S8'!$E$6:$E$23,"Ambos")+SUMIFS('S9'!$I$6:$I$15,'S9'!$B$6:$B$15,$A15,'S9'!$E$6:$E$15,"Víctor")+SUMIFS('S9'!$I$6:$I$15,'S9'!$B$6:$B$15,$A15,'S9'!$E$6:$E$15,"Ambos")+SUMIFS('S10'!$I$6:$I$13,'S10'!$B$6:$B$13,$A15,'S10'!$E$6:$E$13,"Víctor")+SUMIFS('S10'!$I$6:$I$13,'S10'!$B$6:$B$13,$A15,'S10'!$E$6:$E$13,"Ambos")+SUMIFS('Holgura'!$I$6:$I$11,'Holgura'!$B$6:$B$11,$A15,'Holgura'!$E$6:$E$11,"Víctor")+SUMIFS('Holgura'!$I$6:$I$11,'Holgura'!$B$6:$B$11,$A15,'Holgura'!$E$6:$E$11,"Ambos")+SUMIFS('Entrega'!$I$6:$I$9,'Entrega'!$B$6:$B$9,$A15,'Entrega'!$E$6:$E$9,"Víctor")+SUMIFS('Entrega'!$I$6:$I$9,'Entrega'!$B$6:$B$9,$A15,'Entrega'!$E$6:$E$9,"Ambos")+SUMIFS('Defensa'!$I$6:$I$10,'Defensa'!$B$6:$B$10,$A15,'Defensa'!$E$6:$E$10,"Víctor")+SUMIFS('Defensa'!$I$6:$I$10,'Defensa'!$B$6:$B$10,$A15,'Defensa'!$E$6:$E$10,"Ambos")</f>
+        <f>SUMIFS('S1'!$I$6:$I$32,'S1'!$B$6:$B$32,$A15,'S1'!$E$6:$E$32,"Víctor")+SUMIFS('S1'!$I$6:$I$32,'S1'!$B$6:$B$32,$A15,'S1'!$E$6:$E$32,"Ambos")+SUMIFS('S2'!$I$6:$I$23,'S2'!$B$6:$B$23,$A15,'S2'!$E$6:$E$23,"Víctor")+SUMIFS('S2'!$I$6:$I$23,'S2'!$B$6:$B$23,$A15,'S2'!$E$6:$E$23,"Ambos")+SUMIFS('S3'!$I$6:$I$24,'S3'!$B$6:$B$24,$A15,'S3'!$E$6:$E$24,"Víctor")+SUMIFS('S3'!$I$6:$I$24,'S3'!$B$6:$B$24,$A15,'S3'!$E$6:$E$24,"Ambos")+SUMIFS('S4'!$I$6:$I$22,'S4'!$B$6:$B$22,$A15,'S4'!$E$6:$E$22,"Víctor")+SUMIFS('S4'!$I$6:$I$22,'S4'!$B$6:$B$22,$A15,'S4'!$E$6:$E$22,"Ambos")+SUMIFS('S5'!$I$6:$I$20,'S5'!$B$6:$B$20,$A15,'S5'!$E$6:$E$20,"Víctor")+SUMIFS('S5'!$I$6:$I$20,'S5'!$B$6:$B$20,$A15,'S5'!$E$6:$E$20,"Ambos")+SUMIFS('S6'!$I$6:$I$17,'S6'!$B$6:$B$17,$A15,'S6'!$E$6:$E$17,"Víctor")+SUMIFS('S6'!$I$6:$I$17,'S6'!$B$6:$B$17,$A15,'S6'!$E$6:$E$17,"Ambos")+SUMIFS('S7'!$I$6:$I$19,'S7'!$B$6:$B$19,$A15,'S7'!$E$6:$E$19,"Víctor")+SUMIFS('S7'!$I$6:$I$19,'S7'!$B$6:$B$19,$A15,'S7'!$E$6:$E$19,"Ambos")+SUMIFS('S8'!$I$6:$I$23,'S8'!$B$6:$B$23,$A15,'S8'!$E$6:$E$23,"Víctor")+SUMIFS('S8'!$I$6:$I$23,'S8'!$B$6:$B$23,$A15,'S8'!$E$6:$E$23,"Ambos")+SUMIFS('S9'!$I$6:$I$15,'S9'!$B$6:$B$15,$A15,'S9'!$E$6:$E$15,"Víctor")+SUMIFS('S9'!$I$6:$I$15,'S9'!$B$6:$B$15,$A15,'S9'!$E$6:$E$15,"Ambos")+SUMIFS('S10'!$I$6:$I$13,'S10'!$B$6:$B$13,$A15,'S10'!$E$6:$E$13,"Víctor")+SUMIFS('S10'!$I$6:$I$13,'S10'!$B$6:$B$13,$A15,'S10'!$E$6:$E$13,"Ambos")+SUMIFS('Holgura'!$I$6:$I$11,'Holgura'!$B$6:$B$11,$A15,'Holgura'!$E$6:$E$11,"Víctor")+SUMIFS('Holgura'!$I$6:$I$11,'Holgura'!$B$6:$B$11,$A15,'Holgura'!$E$6:$E$11,"Ambos")+SUMIFS('Entrega'!$I$6:$I$9,'Entrega'!$B$6:$B$9,$A15,'Entrega'!$E$6:$E$9,"Víctor")+SUMIFS('Entrega'!$I$6:$I$9,'Entrega'!$B$6:$B$9,$A15,'Entrega'!$E$6:$E$9,"Ambos")+SUMIFS('Defensa'!$I$6:$I$10,'Defensa'!$B$6:$B$10,$A15,'Defensa'!$E$6:$E$10,"Víctor")+SUMIFS('Defensa'!$I$6:$I$10,'Defensa'!$B$6:$B$10,$A15,'Defensa'!$E$6:$E$10,"Ambos")</f>
         <v/>
       </c>
       <c r="E15" s="21">
-        <f>SUMIFS('S1'!$I$6:$I$32,'S1'!$B$6:$B$32,$A15,'S1'!$E$6:$E$32,"Diego")+SUMIFS('S1'!$I$6:$I$32,'S1'!$B$6:$B$32,$A15,'S1'!$E$6:$E$32,"Ambos")+SUMIFS('S2'!$I$6:$I$23,'S2'!$B$6:$B$23,$A15,'S2'!$E$6:$E$23,"Diego")+SUMIFS('S2'!$I$6:$I$23,'S2'!$B$6:$B$23,$A15,'S2'!$E$6:$E$23,"Ambos")+SUMIFS('S3'!$I$6:$I$19,'S3'!$B$6:$B$19,$A15,'S3'!$E$6:$E$19,"Diego")+SUMIFS('S3'!$I$6:$I$19,'S3'!$B$6:$B$19,$A15,'S3'!$E$6:$E$19,"Ambos")+SUMIFS('S4'!$I$6:$I$20,'S4'!$B$6:$B$20,$A15,'S4'!$E$6:$E$20,"Diego")+SUMIFS('S4'!$I$6:$I$20,'S4'!$B$6:$B$20,$A15,'S4'!$E$6:$E$20,"Ambos")+SUMIFS('S5'!$I$6:$I$20,'S5'!$B$6:$B$20,$A15,'S5'!$E$6:$E$20,"Diego")+SUMIFS('S5'!$I$6:$I$20,'S5'!$B$6:$B$20,$A15,'S5'!$E$6:$E$20,"Ambos")+SUMIFS('S6'!$I$6:$I$17,'S6'!$B$6:$B$17,$A15,'S6'!$E$6:$E$17,"Diego")+SUMIFS('S6'!$I$6:$I$17,'S6'!$B$6:$B$17,$A15,'S6'!$E$6:$E$17,"Ambos")+SUMIFS('S7'!$I$6:$I$19,'S7'!$B$6:$B$19,$A15,'S7'!$E$6:$E$19,"Diego")+SUMIFS('S7'!$I$6:$I$19,'S7'!$B$6:$B$19,$A15,'S7'!$E$6:$E$19,"Ambos")+SUMIFS('S8'!$I$6:$I$23,'S8'!$B$6:$B$23,$A15,'S8'!$E$6:$E$23,"Diego")+SUMIFS('S8'!$I$6:$I$23,'S8'!$B$6:$B$23,$A15,'S8'!$E$6:$E$23,"Ambos")+SUMIFS('S9'!$I$6:$I$15,'S9'!$B$6:$B$15,$A15,'S9'!$E$6:$E$15,"Diego")+SUMIFS('S9'!$I$6:$I$15,'S9'!$B$6:$B$15,$A15,'S9'!$E$6:$E$15,"Ambos")+SUMIFS('S10'!$I$6:$I$13,'S10'!$B$6:$B$13,$A15,'S10'!$E$6:$E$13,"Diego")+SUMIFS('S10'!$I$6:$I$13,'S10'!$B$6:$B$13,$A15,'S10'!$E$6:$E$13,"Ambos")+SUMIFS('Holgura'!$I$6:$I$11,'Holgura'!$B$6:$B$11,$A15,'Holgura'!$E$6:$E$11,"Diego")+SUMIFS('Holgura'!$I$6:$I$11,'Holgura'!$B$6:$B$11,$A15,'Holgura'!$E$6:$E$11,"Ambos")+SUMIFS('Entrega'!$I$6:$I$9,'Entrega'!$B$6:$B$9,$A15,'Entrega'!$E$6:$E$9,"Diego")+SUMIFS('Entrega'!$I$6:$I$9,'Entrega'!$B$6:$B$9,$A15,'Entrega'!$E$6:$E$9,"Ambos")+SUMIFS('Defensa'!$I$6:$I$10,'Defensa'!$B$6:$B$10,$A15,'Defensa'!$E$6:$E$10,"Diego")+SUMIFS('Defensa'!$I$6:$I$10,'Defensa'!$B$6:$B$10,$A15,'Defensa'!$E$6:$E$10,"Ambos")</f>
+        <f>SUMIFS('S1'!$I$6:$I$32,'S1'!$B$6:$B$32,$A15,'S1'!$E$6:$E$32,"Diego")+SUMIFS('S1'!$I$6:$I$32,'S1'!$B$6:$B$32,$A15,'S1'!$E$6:$E$32,"Ambos")+SUMIFS('S2'!$I$6:$I$23,'S2'!$B$6:$B$23,$A15,'S2'!$E$6:$E$23,"Diego")+SUMIFS('S2'!$I$6:$I$23,'S2'!$B$6:$B$23,$A15,'S2'!$E$6:$E$23,"Ambos")+SUMIFS('S3'!$I$6:$I$24,'S3'!$B$6:$B$24,$A15,'S3'!$E$6:$E$24,"Diego")+SUMIFS('S3'!$I$6:$I$24,'S3'!$B$6:$B$24,$A15,'S3'!$E$6:$E$24,"Ambos")+SUMIFS('S4'!$I$6:$I$22,'S4'!$B$6:$B$22,$A15,'S4'!$E$6:$E$22,"Diego")+SUMIFS('S4'!$I$6:$I$22,'S4'!$B$6:$B$22,$A15,'S4'!$E$6:$E$22,"Ambos")+SUMIFS('S5'!$I$6:$I$20,'S5'!$B$6:$B$20,$A15,'S5'!$E$6:$E$20,"Diego")+SUMIFS('S5'!$I$6:$I$20,'S5'!$B$6:$B$20,$A15,'S5'!$E$6:$E$20,"Ambos")+SUMIFS('S6'!$I$6:$I$17,'S6'!$B$6:$B$17,$A15,'S6'!$E$6:$E$17,"Diego")+SUMIFS('S6'!$I$6:$I$17,'S6'!$B$6:$B$17,$A15,'S6'!$E$6:$E$17,"Ambos")+SUMIFS('S7'!$I$6:$I$19,'S7'!$B$6:$B$19,$A15,'S7'!$E$6:$E$19,"Diego")+SUMIFS('S7'!$I$6:$I$19,'S7'!$B$6:$B$19,$A15,'S7'!$E$6:$E$19,"Ambos")+SUMIFS('S8'!$I$6:$I$23,'S8'!$B$6:$B$23,$A15,'S8'!$E$6:$E$23,"Diego")+SUMIFS('S8'!$I$6:$I$23,'S8'!$B$6:$B$23,$A15,'S8'!$E$6:$E$23,"Ambos")+SUMIFS('S9'!$I$6:$I$15,'S9'!$B$6:$B$15,$A15,'S9'!$E$6:$E$15,"Diego")+SUMIFS('S9'!$I$6:$I$15,'S9'!$B$6:$B$15,$A15,'S9'!$E$6:$E$15,"Ambos")+SUMIFS('S10'!$I$6:$I$13,'S10'!$B$6:$B$13,$A15,'S10'!$E$6:$E$13,"Diego")+SUMIFS('S10'!$I$6:$I$13,'S10'!$B$6:$B$13,$A15,'S10'!$E$6:$E$13,"Ambos")+SUMIFS('Holgura'!$I$6:$I$11,'Holgura'!$B$6:$B$11,$A15,'Holgura'!$E$6:$E$11,"Diego")+SUMIFS('Holgura'!$I$6:$I$11,'Holgura'!$B$6:$B$11,$A15,'Holgura'!$E$6:$E$11,"Ambos")+SUMIFS('Entrega'!$I$6:$I$9,'Entrega'!$B$6:$B$9,$A15,'Entrega'!$E$6:$E$9,"Diego")+SUMIFS('Entrega'!$I$6:$I$9,'Entrega'!$B$6:$B$9,$A15,'Entrega'!$E$6:$E$9,"Ambos")+SUMIFS('Defensa'!$I$6:$I$10,'Defensa'!$B$6:$B$10,$A15,'Defensa'!$E$6:$E$10,"Diego")+SUMIFS('Defensa'!$I$6:$I$10,'Defensa'!$B$6:$B$10,$A15,'Defensa'!$E$6:$E$10,"Ambos")</f>
         <v/>
       </c>
       <c r="F15" s="21">
-        <f>COUNTIFS('S1'!$B$6:$B$32,$A15,'S1'!$E$6:$E$32,"Víctor")+COUNTIFS('S1'!$B$6:$B$32,$A15,'S1'!$E$6:$E$32,"Ambos")+COUNTIFS('S2'!$B$6:$B$23,$A15,'S2'!$E$6:$E$23,"Víctor")+COUNTIFS('S2'!$B$6:$B$23,$A15,'S2'!$E$6:$E$23,"Ambos")+COUNTIFS('S3'!$B$6:$B$19,$A15,'S3'!$E$6:$E$19,"Víctor")+COUNTIFS('S3'!$B$6:$B$19,$A15,'S3'!$E$6:$E$19,"Ambos")+COUNTIFS('S4'!$B$6:$B$20,$A15,'S4'!$E$6:$E$20,"Víctor")+COUNTIFS('S4'!$B$6:$B$20,$A15,'S4'!$E$6:$E$20,"Ambos")+COUNTIFS('S5'!$B$6:$B$20,$A15,'S5'!$E$6:$E$20,"Víctor")+COUNTIFS('S5'!$B$6:$B$20,$A15,'S5'!$E$6:$E$20,"Ambos")+COUNTIFS('S6'!$B$6:$B$17,$A15,'S6'!$E$6:$E$17,"Víctor")+COUNTIFS('S6'!$B$6:$B$17,$A15,'S6'!$E$6:$E$17,"Ambos")+COUNTIFS('S7'!$B$6:$B$19,$A15,'S7'!$E$6:$E$19,"Víctor")+COUNTIFS('S7'!$B$6:$B$19,$A15,'S7'!$E$6:$E$19,"Ambos")+COUNTIFS('S8'!$B$6:$B$23,$A15,'S8'!$E$6:$E$23,"Víctor")+COUNTIFS('S8'!$B$6:$B$23,$A15,'S8'!$E$6:$E$23,"Ambos")+COUNTIFS('S9'!$B$6:$B$15,$A15,'S9'!$E$6:$E$15,"Víctor")+COUNTIFS('S9'!$B$6:$B$15,$A15,'S9'!$E$6:$E$15,"Ambos")+COUNTIFS('S10'!$B$6:$B$13,$A15,'S10'!$E$6:$E$13,"Víctor")+COUNTIFS('S10'!$B$6:$B$13,$A15,'S10'!$E$6:$E$13,"Ambos")+COUNTIFS('Holgura'!$B$6:$B$11,$A15,'Holgura'!$E$6:$E$11,"Víctor")+COUNTIFS('Holgura'!$B$6:$B$11,$A15,'Holgura'!$E$6:$E$11,"Ambos")+COUNTIFS('Entrega'!$B$6:$B$9,$A15,'Entrega'!$E$6:$E$9,"Víctor")+COUNTIFS('Entrega'!$B$6:$B$9,$A15,'Entrega'!$E$6:$E$9,"Ambos")+COUNTIFS('Defensa'!$B$6:$B$10,$A15,'Defensa'!$E$6:$E$10,"Víctor")+COUNTIFS('Defensa'!$B$6:$B$10,$A15,'Defensa'!$E$6:$E$10,"Ambos")</f>
+        <f>COUNTIFS('S1'!$B$6:$B$32,$A15,'S1'!$E$6:$E$32,"Víctor")+COUNTIFS('S1'!$B$6:$B$32,$A15,'S1'!$E$6:$E$32,"Ambos")+COUNTIFS('S2'!$B$6:$B$23,$A15,'S2'!$E$6:$E$23,"Víctor")+COUNTIFS('S2'!$B$6:$B$23,$A15,'S2'!$E$6:$E$23,"Ambos")+COUNTIFS('S3'!$B$6:$B$24,$A15,'S3'!$E$6:$E$24,"Víctor")+COUNTIFS('S3'!$B$6:$B$24,$A15,'S3'!$E$6:$E$24,"Ambos")+COUNTIFS('S4'!$B$6:$B$22,$A15,'S4'!$E$6:$E$22,"Víctor")+COUNTIFS('S4'!$B$6:$B$22,$A15,'S4'!$E$6:$E$22,"Ambos")+COUNTIFS('S5'!$B$6:$B$20,$A15,'S5'!$E$6:$E$20,"Víctor")+COUNTIFS('S5'!$B$6:$B$20,$A15,'S5'!$E$6:$E$20,"Ambos")+COUNTIFS('S6'!$B$6:$B$17,$A15,'S6'!$E$6:$E$17,"Víctor")+COUNTIFS('S6'!$B$6:$B$17,$A15,'S6'!$E$6:$E$17,"Ambos")+COUNTIFS('S7'!$B$6:$B$19,$A15,'S7'!$E$6:$E$19,"Víctor")+COUNTIFS('S7'!$B$6:$B$19,$A15,'S7'!$E$6:$E$19,"Ambos")+COUNTIFS('S8'!$B$6:$B$23,$A15,'S8'!$E$6:$E$23,"Víctor")+COUNTIFS('S8'!$B$6:$B$23,$A15,'S8'!$E$6:$E$23,"Ambos")+COUNTIFS('S9'!$B$6:$B$15,$A15,'S9'!$E$6:$E$15,"Víctor")+COUNTIFS('S9'!$B$6:$B$15,$A15,'S9'!$E$6:$E$15,"Ambos")+COUNTIFS('S10'!$B$6:$B$13,$A15,'S10'!$E$6:$E$13,"Víctor")+COUNTIFS('S10'!$B$6:$B$13,$A15,'S10'!$E$6:$E$13,"Ambos")+COUNTIFS('Holgura'!$B$6:$B$11,$A15,'Holgura'!$E$6:$E$11,"Víctor")+COUNTIFS('Holgura'!$B$6:$B$11,$A15,'Holgura'!$E$6:$E$11,"Ambos")+COUNTIFS('Entrega'!$B$6:$B$9,$A15,'Entrega'!$E$6:$E$9,"Víctor")+COUNTIFS('Entrega'!$B$6:$B$9,$A15,'Entrega'!$E$6:$E$9,"Ambos")+COUNTIFS('Defensa'!$B$6:$B$10,$A15,'Defensa'!$E$6:$E$10,"Víctor")+COUNTIFS('Defensa'!$B$6:$B$10,$A15,'Defensa'!$E$6:$E$10,"Ambos")</f>
         <v/>
       </c>
       <c r="G15" s="21">
-        <f>COUNTIFS('S1'!$B$6:$B$32,$A15,'S1'!$E$6:$E$32,"Diego")+COUNTIFS('S1'!$B$6:$B$32,$A15,'S1'!$E$6:$E$32,"Ambos")+COUNTIFS('S2'!$B$6:$B$23,$A15,'S2'!$E$6:$E$23,"Diego")+COUNTIFS('S2'!$B$6:$B$23,$A15,'S2'!$E$6:$E$23,"Ambos")+COUNTIFS('S3'!$B$6:$B$19,$A15,'S3'!$E$6:$E$19,"Diego")+COUNTIFS('S3'!$B$6:$B$19,$A15,'S3'!$E$6:$E$19,"Ambos")+COUNTIFS('S4'!$B$6:$B$20,$A15,'S4'!$E$6:$E$20,"Diego")+COUNTIFS('S4'!$B$6:$B$20,$A15,'S4'!$E$6:$E$20,"Ambos")+COUNTIFS('S5'!$B$6:$B$20,$A15,'S5'!$E$6:$E$20,"Diego")+COUNTIFS('S5'!$B$6:$B$20,$A15,'S5'!$E$6:$E$20,"Ambos")+COUNTIFS('S6'!$B$6:$B$17,$A15,'S6'!$E$6:$E$17,"Diego")+COUNTIFS('S6'!$B$6:$B$17,$A15,'S6'!$E$6:$E$17,"Ambos")+COUNTIFS('S7'!$B$6:$B$19,$A15,'S7'!$E$6:$E$19,"Diego")+COUNTIFS('S7'!$B$6:$B$19,$A15,'S7'!$E$6:$E$19,"Ambos")+COUNTIFS('S8'!$B$6:$B$23,$A15,'S8'!$E$6:$E$23,"Diego")+COUNTIFS('S8'!$B$6:$B$23,$A15,'S8'!$E$6:$E$23,"Ambos")+COUNTIFS('S9'!$B$6:$B$15,$A15,'S9'!$E$6:$E$15,"Diego")+COUNTIFS('S9'!$B$6:$B$15,$A15,'S9'!$E$6:$E$15,"Ambos")+COUNTIFS('S10'!$B$6:$B$13,$A15,'S10'!$E$6:$E$13,"Diego")+COUNTIFS('S10'!$B$6:$B$13,$A15,'S10'!$E$6:$E$13,"Ambos")+COUNTIFS('Holgura'!$B$6:$B$11,$A15,'Holgura'!$E$6:$E$11,"Diego")+COUNTIFS('Holgura'!$B$6:$B$11,$A15,'Holgura'!$E$6:$E$11,"Ambos")+COUNTIFS('Entrega'!$B$6:$B$9,$A15,'Entrega'!$E$6:$E$9,"Diego")+COUNTIFS('Entrega'!$B$6:$B$9,$A15,'Entrega'!$E$6:$E$9,"Ambos")+COUNTIFS('Defensa'!$B$6:$B$10,$A15,'Defensa'!$E$6:$E$10,"Diego")+COUNTIFS('Defensa'!$B$6:$B$10,$A15,'Defensa'!$E$6:$E$10,"Ambos")</f>
+        <f>COUNTIFS('S1'!$B$6:$B$32,$A15,'S1'!$E$6:$E$32,"Diego")+COUNTIFS('S1'!$B$6:$B$32,$A15,'S1'!$E$6:$E$32,"Ambos")+COUNTIFS('S2'!$B$6:$B$23,$A15,'S2'!$E$6:$E$23,"Diego")+COUNTIFS('S2'!$B$6:$B$23,$A15,'S2'!$E$6:$E$23,"Ambos")+COUNTIFS('S3'!$B$6:$B$24,$A15,'S3'!$E$6:$E$24,"Diego")+COUNTIFS('S3'!$B$6:$B$24,$A15,'S3'!$E$6:$E$24,"Ambos")+COUNTIFS('S4'!$B$6:$B$22,$A15,'S4'!$E$6:$E$22,"Diego")+COUNTIFS('S4'!$B$6:$B$22,$A15,'S4'!$E$6:$E$22,"Ambos")+COUNTIFS('S5'!$B$6:$B$20,$A15,'S5'!$E$6:$E$20,"Diego")+COUNTIFS('S5'!$B$6:$B$20,$A15,'S5'!$E$6:$E$20,"Ambos")+COUNTIFS('S6'!$B$6:$B$17,$A15,'S6'!$E$6:$E$17,"Diego")+COUNTIFS('S6'!$B$6:$B$17,$A15,'S6'!$E$6:$E$17,"Ambos")+COUNTIFS('S7'!$B$6:$B$19,$A15,'S7'!$E$6:$E$19,"Diego")+COUNTIFS('S7'!$B$6:$B$19,$A15,'S7'!$E$6:$E$19,"Ambos")+COUNTIFS('S8'!$B$6:$B$23,$A15,'S8'!$E$6:$E$23,"Diego")+COUNTIFS('S8'!$B$6:$B$23,$A15,'S8'!$E$6:$E$23,"Ambos")+COUNTIFS('S9'!$B$6:$B$15,$A15,'S9'!$E$6:$E$15,"Diego")+COUNTIFS('S9'!$B$6:$B$15,$A15,'S9'!$E$6:$E$15,"Ambos")+COUNTIFS('S10'!$B$6:$B$13,$A15,'S10'!$E$6:$E$13,"Diego")+COUNTIFS('S10'!$B$6:$B$13,$A15,'S10'!$E$6:$E$13,"Ambos")+COUNTIFS('Holgura'!$B$6:$B$11,$A15,'Holgura'!$E$6:$E$11,"Diego")+COUNTIFS('Holgura'!$B$6:$B$11,$A15,'Holgura'!$E$6:$E$11,"Ambos")+COUNTIFS('Entrega'!$B$6:$B$9,$A15,'Entrega'!$E$6:$E$9,"Diego")+COUNTIFS('Entrega'!$B$6:$B$9,$A15,'Entrega'!$E$6:$E$9,"Ambos")+COUNTIFS('Defensa'!$B$6:$B$10,$A15,'Defensa'!$E$6:$E$10,"Diego")+COUNTIFS('Defensa'!$B$6:$B$10,$A15,'Defensa'!$E$6:$E$10,"Ambos")</f>
         <v/>
       </c>
     </row>
@@ -8999,19 +9020,19 @@
         <v/>
       </c>
       <c r="D16" s="21">
-        <f>SUMIFS('S1'!$I$6:$I$32,'S1'!$B$6:$B$32,$A16,'S1'!$E$6:$E$32,"Víctor")+SUMIFS('S1'!$I$6:$I$32,'S1'!$B$6:$B$32,$A16,'S1'!$E$6:$E$32,"Ambos")+SUMIFS('S2'!$I$6:$I$23,'S2'!$B$6:$B$23,$A16,'S2'!$E$6:$E$23,"Víctor")+SUMIFS('S2'!$I$6:$I$23,'S2'!$B$6:$B$23,$A16,'S2'!$E$6:$E$23,"Ambos")+SUMIFS('S3'!$I$6:$I$19,'S3'!$B$6:$B$19,$A16,'S3'!$E$6:$E$19,"Víctor")+SUMIFS('S3'!$I$6:$I$19,'S3'!$B$6:$B$19,$A16,'S3'!$E$6:$E$19,"Ambos")+SUMIFS('S4'!$I$6:$I$20,'S4'!$B$6:$B$20,$A16,'S4'!$E$6:$E$20,"Víctor")+SUMIFS('S4'!$I$6:$I$20,'S4'!$B$6:$B$20,$A16,'S4'!$E$6:$E$20,"Ambos")+SUMIFS('S5'!$I$6:$I$20,'S5'!$B$6:$B$20,$A16,'S5'!$E$6:$E$20,"Víctor")+SUMIFS('S5'!$I$6:$I$20,'S5'!$B$6:$B$20,$A16,'S5'!$E$6:$E$20,"Ambos")+SUMIFS('S6'!$I$6:$I$17,'S6'!$B$6:$B$17,$A16,'S6'!$E$6:$E$17,"Víctor")+SUMIFS('S6'!$I$6:$I$17,'S6'!$B$6:$B$17,$A16,'S6'!$E$6:$E$17,"Ambos")+SUMIFS('S7'!$I$6:$I$19,'S7'!$B$6:$B$19,$A16,'S7'!$E$6:$E$19,"Víctor")+SUMIFS('S7'!$I$6:$I$19,'S7'!$B$6:$B$19,$A16,'S7'!$E$6:$E$19,"Ambos")+SUMIFS('S8'!$I$6:$I$23,'S8'!$B$6:$B$23,$A16,'S8'!$E$6:$E$23,"Víctor")+SUMIFS('S8'!$I$6:$I$23,'S8'!$B$6:$B$23,$A16,'S8'!$E$6:$E$23,"Ambos")+SUMIFS('S9'!$I$6:$I$15,'S9'!$B$6:$B$15,$A16,'S9'!$E$6:$E$15,"Víctor")+SUMIFS('S9'!$I$6:$I$15,'S9'!$B$6:$B$15,$A16,'S9'!$E$6:$E$15,"Ambos")+SUMIFS('S10'!$I$6:$I$13,'S10'!$B$6:$B$13,$A16,'S10'!$E$6:$E$13,"Víctor")+SUMIFS('S10'!$I$6:$I$13,'S10'!$B$6:$B$13,$A16,'S10'!$E$6:$E$13,"Ambos")+SUMIFS('Holgura'!$I$6:$I$11,'Holgura'!$B$6:$B$11,$A16,'Holgura'!$E$6:$E$11,"Víctor")+SUMIFS('Holgura'!$I$6:$I$11,'Holgura'!$B$6:$B$11,$A16,'Holgura'!$E$6:$E$11,"Ambos")+SUMIFS('Entrega'!$I$6:$I$9,'Entrega'!$B$6:$B$9,$A16,'Entrega'!$E$6:$E$9,"Víctor")+SUMIFS('Entrega'!$I$6:$I$9,'Entrega'!$B$6:$B$9,$A16,'Entrega'!$E$6:$E$9,"Ambos")+SUMIFS('Defensa'!$I$6:$I$10,'Defensa'!$B$6:$B$10,$A16,'Defensa'!$E$6:$E$10,"Víctor")+SUMIFS('Defensa'!$I$6:$I$10,'Defensa'!$B$6:$B$10,$A16,'Defensa'!$E$6:$E$10,"Ambos")</f>
+        <f>SUMIFS('S1'!$I$6:$I$32,'S1'!$B$6:$B$32,$A16,'S1'!$E$6:$E$32,"Víctor")+SUMIFS('S1'!$I$6:$I$32,'S1'!$B$6:$B$32,$A16,'S1'!$E$6:$E$32,"Ambos")+SUMIFS('S2'!$I$6:$I$23,'S2'!$B$6:$B$23,$A16,'S2'!$E$6:$E$23,"Víctor")+SUMIFS('S2'!$I$6:$I$23,'S2'!$B$6:$B$23,$A16,'S2'!$E$6:$E$23,"Ambos")+SUMIFS('S3'!$I$6:$I$24,'S3'!$B$6:$B$24,$A16,'S3'!$E$6:$E$24,"Víctor")+SUMIFS('S3'!$I$6:$I$24,'S3'!$B$6:$B$24,$A16,'S3'!$E$6:$E$24,"Ambos")+SUMIFS('S4'!$I$6:$I$22,'S4'!$B$6:$B$22,$A16,'S4'!$E$6:$E$22,"Víctor")+SUMIFS('S4'!$I$6:$I$22,'S4'!$B$6:$B$22,$A16,'S4'!$E$6:$E$22,"Ambos")+SUMIFS('S5'!$I$6:$I$20,'S5'!$B$6:$B$20,$A16,'S5'!$E$6:$E$20,"Víctor")+SUMIFS('S5'!$I$6:$I$20,'S5'!$B$6:$B$20,$A16,'S5'!$E$6:$E$20,"Ambos")+SUMIFS('S6'!$I$6:$I$17,'S6'!$B$6:$B$17,$A16,'S6'!$E$6:$E$17,"Víctor")+SUMIFS('S6'!$I$6:$I$17,'S6'!$B$6:$B$17,$A16,'S6'!$E$6:$E$17,"Ambos")+SUMIFS('S7'!$I$6:$I$19,'S7'!$B$6:$B$19,$A16,'S7'!$E$6:$E$19,"Víctor")+SUMIFS('S7'!$I$6:$I$19,'S7'!$B$6:$B$19,$A16,'S7'!$E$6:$E$19,"Ambos")+SUMIFS('S8'!$I$6:$I$23,'S8'!$B$6:$B$23,$A16,'S8'!$E$6:$E$23,"Víctor")+SUMIFS('S8'!$I$6:$I$23,'S8'!$B$6:$B$23,$A16,'S8'!$E$6:$E$23,"Ambos")+SUMIFS('S9'!$I$6:$I$15,'S9'!$B$6:$B$15,$A16,'S9'!$E$6:$E$15,"Víctor")+SUMIFS('S9'!$I$6:$I$15,'S9'!$B$6:$B$15,$A16,'S9'!$E$6:$E$15,"Ambos")+SUMIFS('S10'!$I$6:$I$13,'S10'!$B$6:$B$13,$A16,'S10'!$E$6:$E$13,"Víctor")+SUMIFS('S10'!$I$6:$I$13,'S10'!$B$6:$B$13,$A16,'S10'!$E$6:$E$13,"Ambos")+SUMIFS('Holgura'!$I$6:$I$11,'Holgura'!$B$6:$B$11,$A16,'Holgura'!$E$6:$E$11,"Víctor")+SUMIFS('Holgura'!$I$6:$I$11,'Holgura'!$B$6:$B$11,$A16,'Holgura'!$E$6:$E$11,"Ambos")+SUMIFS('Entrega'!$I$6:$I$9,'Entrega'!$B$6:$B$9,$A16,'Entrega'!$E$6:$E$9,"Víctor")+SUMIFS('Entrega'!$I$6:$I$9,'Entrega'!$B$6:$B$9,$A16,'Entrega'!$E$6:$E$9,"Ambos")+SUMIFS('Defensa'!$I$6:$I$10,'Defensa'!$B$6:$B$10,$A16,'Defensa'!$E$6:$E$10,"Víctor")+SUMIFS('Defensa'!$I$6:$I$10,'Defensa'!$B$6:$B$10,$A16,'Defensa'!$E$6:$E$10,"Ambos")</f>
         <v/>
       </c>
       <c r="E16" s="21">
-        <f>SUMIFS('S1'!$I$6:$I$32,'S1'!$B$6:$B$32,$A16,'S1'!$E$6:$E$32,"Diego")+SUMIFS('S1'!$I$6:$I$32,'S1'!$B$6:$B$32,$A16,'S1'!$E$6:$E$32,"Ambos")+SUMIFS('S2'!$I$6:$I$23,'S2'!$B$6:$B$23,$A16,'S2'!$E$6:$E$23,"Diego")+SUMIFS('S2'!$I$6:$I$23,'S2'!$B$6:$B$23,$A16,'S2'!$E$6:$E$23,"Ambos")+SUMIFS('S3'!$I$6:$I$19,'S3'!$B$6:$B$19,$A16,'S3'!$E$6:$E$19,"Diego")+SUMIFS('S3'!$I$6:$I$19,'S3'!$B$6:$B$19,$A16,'S3'!$E$6:$E$19,"Ambos")+SUMIFS('S4'!$I$6:$I$20,'S4'!$B$6:$B$20,$A16,'S4'!$E$6:$E$20,"Diego")+SUMIFS('S4'!$I$6:$I$20,'S4'!$B$6:$B$20,$A16,'S4'!$E$6:$E$20,"Ambos")+SUMIFS('S5'!$I$6:$I$20,'S5'!$B$6:$B$20,$A16,'S5'!$E$6:$E$20,"Diego")+SUMIFS('S5'!$I$6:$I$20,'S5'!$B$6:$B$20,$A16,'S5'!$E$6:$E$20,"Ambos")+SUMIFS('S6'!$I$6:$I$17,'S6'!$B$6:$B$17,$A16,'S6'!$E$6:$E$17,"Diego")+SUMIFS('S6'!$I$6:$I$17,'S6'!$B$6:$B$17,$A16,'S6'!$E$6:$E$17,"Ambos")+SUMIFS('S7'!$I$6:$I$19,'S7'!$B$6:$B$19,$A16,'S7'!$E$6:$E$19,"Diego")+SUMIFS('S7'!$I$6:$I$19,'S7'!$B$6:$B$19,$A16,'S7'!$E$6:$E$19,"Ambos")+SUMIFS('S8'!$I$6:$I$23,'S8'!$B$6:$B$23,$A16,'S8'!$E$6:$E$23,"Diego")+SUMIFS('S8'!$I$6:$I$23,'S8'!$B$6:$B$23,$A16,'S8'!$E$6:$E$23,"Ambos")+SUMIFS('S9'!$I$6:$I$15,'S9'!$B$6:$B$15,$A16,'S9'!$E$6:$E$15,"Diego")+SUMIFS('S9'!$I$6:$I$15,'S9'!$B$6:$B$15,$A16,'S9'!$E$6:$E$15,"Ambos")+SUMIFS('S10'!$I$6:$I$13,'S10'!$B$6:$B$13,$A16,'S10'!$E$6:$E$13,"Diego")+SUMIFS('S10'!$I$6:$I$13,'S10'!$B$6:$B$13,$A16,'S10'!$E$6:$E$13,"Ambos")+SUMIFS('Holgura'!$I$6:$I$11,'Holgura'!$B$6:$B$11,$A16,'Holgura'!$E$6:$E$11,"Diego")+SUMIFS('Holgura'!$I$6:$I$11,'Holgura'!$B$6:$B$11,$A16,'Holgura'!$E$6:$E$11,"Ambos")+SUMIFS('Entrega'!$I$6:$I$9,'Entrega'!$B$6:$B$9,$A16,'Entrega'!$E$6:$E$9,"Diego")+SUMIFS('Entrega'!$I$6:$I$9,'Entrega'!$B$6:$B$9,$A16,'Entrega'!$E$6:$E$9,"Ambos")+SUMIFS('Defensa'!$I$6:$I$10,'Defensa'!$B$6:$B$10,$A16,'Defensa'!$E$6:$E$10,"Diego")+SUMIFS('Defensa'!$I$6:$I$10,'Defensa'!$B$6:$B$10,$A16,'Defensa'!$E$6:$E$10,"Ambos")</f>
+        <f>SUMIFS('S1'!$I$6:$I$32,'S1'!$B$6:$B$32,$A16,'S1'!$E$6:$E$32,"Diego")+SUMIFS('S1'!$I$6:$I$32,'S1'!$B$6:$B$32,$A16,'S1'!$E$6:$E$32,"Ambos")+SUMIFS('S2'!$I$6:$I$23,'S2'!$B$6:$B$23,$A16,'S2'!$E$6:$E$23,"Diego")+SUMIFS('S2'!$I$6:$I$23,'S2'!$B$6:$B$23,$A16,'S2'!$E$6:$E$23,"Ambos")+SUMIFS('S3'!$I$6:$I$24,'S3'!$B$6:$B$24,$A16,'S3'!$E$6:$E$24,"Diego")+SUMIFS('S3'!$I$6:$I$24,'S3'!$B$6:$B$24,$A16,'S3'!$E$6:$E$24,"Ambos")+SUMIFS('S4'!$I$6:$I$22,'S4'!$B$6:$B$22,$A16,'S4'!$E$6:$E$22,"Diego")+SUMIFS('S4'!$I$6:$I$22,'S4'!$B$6:$B$22,$A16,'S4'!$E$6:$E$22,"Ambos")+SUMIFS('S5'!$I$6:$I$20,'S5'!$B$6:$B$20,$A16,'S5'!$E$6:$E$20,"Diego")+SUMIFS('S5'!$I$6:$I$20,'S5'!$B$6:$B$20,$A16,'S5'!$E$6:$E$20,"Ambos")+SUMIFS('S6'!$I$6:$I$17,'S6'!$B$6:$B$17,$A16,'S6'!$E$6:$E$17,"Diego")+SUMIFS('S6'!$I$6:$I$17,'S6'!$B$6:$B$17,$A16,'S6'!$E$6:$E$17,"Ambos")+SUMIFS('S7'!$I$6:$I$19,'S7'!$B$6:$B$19,$A16,'S7'!$E$6:$E$19,"Diego")+SUMIFS('S7'!$I$6:$I$19,'S7'!$B$6:$B$19,$A16,'S7'!$E$6:$E$19,"Ambos")+SUMIFS('S8'!$I$6:$I$23,'S8'!$B$6:$B$23,$A16,'S8'!$E$6:$E$23,"Diego")+SUMIFS('S8'!$I$6:$I$23,'S8'!$B$6:$B$23,$A16,'S8'!$E$6:$E$23,"Ambos")+SUMIFS('S9'!$I$6:$I$15,'S9'!$B$6:$B$15,$A16,'S9'!$E$6:$E$15,"Diego")+SUMIFS('S9'!$I$6:$I$15,'S9'!$B$6:$B$15,$A16,'S9'!$E$6:$E$15,"Ambos")+SUMIFS('S10'!$I$6:$I$13,'S10'!$B$6:$B$13,$A16,'S10'!$E$6:$E$13,"Diego")+SUMIFS('S10'!$I$6:$I$13,'S10'!$B$6:$B$13,$A16,'S10'!$E$6:$E$13,"Ambos")+SUMIFS('Holgura'!$I$6:$I$11,'Holgura'!$B$6:$B$11,$A16,'Holgura'!$E$6:$E$11,"Diego")+SUMIFS('Holgura'!$I$6:$I$11,'Holgura'!$B$6:$B$11,$A16,'Holgura'!$E$6:$E$11,"Ambos")+SUMIFS('Entrega'!$I$6:$I$9,'Entrega'!$B$6:$B$9,$A16,'Entrega'!$E$6:$E$9,"Diego")+SUMIFS('Entrega'!$I$6:$I$9,'Entrega'!$B$6:$B$9,$A16,'Entrega'!$E$6:$E$9,"Ambos")+SUMIFS('Defensa'!$I$6:$I$10,'Defensa'!$B$6:$B$10,$A16,'Defensa'!$E$6:$E$10,"Diego")+SUMIFS('Defensa'!$I$6:$I$10,'Defensa'!$B$6:$B$10,$A16,'Defensa'!$E$6:$E$10,"Ambos")</f>
         <v/>
       </c>
       <c r="F16" s="21">
-        <f>COUNTIFS('S1'!$B$6:$B$32,$A16,'S1'!$E$6:$E$32,"Víctor")+COUNTIFS('S1'!$B$6:$B$32,$A16,'S1'!$E$6:$E$32,"Ambos")+COUNTIFS('S2'!$B$6:$B$23,$A16,'S2'!$E$6:$E$23,"Víctor")+COUNTIFS('S2'!$B$6:$B$23,$A16,'S2'!$E$6:$E$23,"Ambos")+COUNTIFS('S3'!$B$6:$B$19,$A16,'S3'!$E$6:$E$19,"Víctor")+COUNTIFS('S3'!$B$6:$B$19,$A16,'S3'!$E$6:$E$19,"Ambos")+COUNTIFS('S4'!$B$6:$B$20,$A16,'S4'!$E$6:$E$20,"Víctor")+COUNTIFS('S4'!$B$6:$B$20,$A16,'S4'!$E$6:$E$20,"Ambos")+COUNTIFS('S5'!$B$6:$B$20,$A16,'S5'!$E$6:$E$20,"Víctor")+COUNTIFS('S5'!$B$6:$B$20,$A16,'S5'!$E$6:$E$20,"Ambos")+COUNTIFS('S6'!$B$6:$B$17,$A16,'S6'!$E$6:$E$17,"Víctor")+COUNTIFS('S6'!$B$6:$B$17,$A16,'S6'!$E$6:$E$17,"Ambos")+COUNTIFS('S7'!$B$6:$B$19,$A16,'S7'!$E$6:$E$19,"Víctor")+COUNTIFS('S7'!$B$6:$B$19,$A16,'S7'!$E$6:$E$19,"Ambos")+COUNTIFS('S8'!$B$6:$B$23,$A16,'S8'!$E$6:$E$23,"Víctor")+COUNTIFS('S8'!$B$6:$B$23,$A16,'S8'!$E$6:$E$23,"Ambos")+COUNTIFS('S9'!$B$6:$B$15,$A16,'S9'!$E$6:$E$15,"Víctor")+COUNTIFS('S9'!$B$6:$B$15,$A16,'S9'!$E$6:$E$15,"Ambos")+COUNTIFS('S10'!$B$6:$B$13,$A16,'S10'!$E$6:$E$13,"Víctor")+COUNTIFS('S10'!$B$6:$B$13,$A16,'S10'!$E$6:$E$13,"Ambos")+COUNTIFS('Holgura'!$B$6:$B$11,$A16,'Holgura'!$E$6:$E$11,"Víctor")+COUNTIFS('Holgura'!$B$6:$B$11,$A16,'Holgura'!$E$6:$E$11,"Ambos")+COUNTIFS('Entrega'!$B$6:$B$9,$A16,'Entrega'!$E$6:$E$9,"Víctor")+COUNTIFS('Entrega'!$B$6:$B$9,$A16,'Entrega'!$E$6:$E$9,"Ambos")+COUNTIFS('Defensa'!$B$6:$B$10,$A16,'Defensa'!$E$6:$E$10,"Víctor")+COUNTIFS('Defensa'!$B$6:$B$10,$A16,'Defensa'!$E$6:$E$10,"Ambos")</f>
+        <f>COUNTIFS('S1'!$B$6:$B$32,$A16,'S1'!$E$6:$E$32,"Víctor")+COUNTIFS('S1'!$B$6:$B$32,$A16,'S1'!$E$6:$E$32,"Ambos")+COUNTIFS('S2'!$B$6:$B$23,$A16,'S2'!$E$6:$E$23,"Víctor")+COUNTIFS('S2'!$B$6:$B$23,$A16,'S2'!$E$6:$E$23,"Ambos")+COUNTIFS('S3'!$B$6:$B$24,$A16,'S3'!$E$6:$E$24,"Víctor")+COUNTIFS('S3'!$B$6:$B$24,$A16,'S3'!$E$6:$E$24,"Ambos")+COUNTIFS('S4'!$B$6:$B$22,$A16,'S4'!$E$6:$E$22,"Víctor")+COUNTIFS('S4'!$B$6:$B$22,$A16,'S4'!$E$6:$E$22,"Ambos")+COUNTIFS('S5'!$B$6:$B$20,$A16,'S5'!$E$6:$E$20,"Víctor")+COUNTIFS('S5'!$B$6:$B$20,$A16,'S5'!$E$6:$E$20,"Ambos")+COUNTIFS('S6'!$B$6:$B$17,$A16,'S6'!$E$6:$E$17,"Víctor")+COUNTIFS('S6'!$B$6:$B$17,$A16,'S6'!$E$6:$E$17,"Ambos")+COUNTIFS('S7'!$B$6:$B$19,$A16,'S7'!$E$6:$E$19,"Víctor")+COUNTIFS('S7'!$B$6:$B$19,$A16,'S7'!$E$6:$E$19,"Ambos")+COUNTIFS('S8'!$B$6:$B$23,$A16,'S8'!$E$6:$E$23,"Víctor")+COUNTIFS('S8'!$B$6:$B$23,$A16,'S8'!$E$6:$E$23,"Ambos")+COUNTIFS('S9'!$B$6:$B$15,$A16,'S9'!$E$6:$E$15,"Víctor")+COUNTIFS('S9'!$B$6:$B$15,$A16,'S9'!$E$6:$E$15,"Ambos")+COUNTIFS('S10'!$B$6:$B$13,$A16,'S10'!$E$6:$E$13,"Víctor")+COUNTIFS('S10'!$B$6:$B$13,$A16,'S10'!$E$6:$E$13,"Ambos")+COUNTIFS('Holgura'!$B$6:$B$11,$A16,'Holgura'!$E$6:$E$11,"Víctor")+COUNTIFS('Holgura'!$B$6:$B$11,$A16,'Holgura'!$E$6:$E$11,"Ambos")+COUNTIFS('Entrega'!$B$6:$B$9,$A16,'Entrega'!$E$6:$E$9,"Víctor")+COUNTIFS('Entrega'!$B$6:$B$9,$A16,'Entrega'!$E$6:$E$9,"Ambos")+COUNTIFS('Defensa'!$B$6:$B$10,$A16,'Defensa'!$E$6:$E$10,"Víctor")+COUNTIFS('Defensa'!$B$6:$B$10,$A16,'Defensa'!$E$6:$E$10,"Ambos")</f>
         <v/>
       </c>
       <c r="G16" s="21">
-        <f>COUNTIFS('S1'!$B$6:$B$32,$A16,'S1'!$E$6:$E$32,"Diego")+COUNTIFS('S1'!$B$6:$B$32,$A16,'S1'!$E$6:$E$32,"Ambos")+COUNTIFS('S2'!$B$6:$B$23,$A16,'S2'!$E$6:$E$23,"Diego")+COUNTIFS('S2'!$B$6:$B$23,$A16,'S2'!$E$6:$E$23,"Ambos")+COUNTIFS('S3'!$B$6:$B$19,$A16,'S3'!$E$6:$E$19,"Diego")+COUNTIFS('S3'!$B$6:$B$19,$A16,'S3'!$E$6:$E$19,"Ambos")+COUNTIFS('S4'!$B$6:$B$20,$A16,'S4'!$E$6:$E$20,"Diego")+COUNTIFS('S4'!$B$6:$B$20,$A16,'S4'!$E$6:$E$20,"Ambos")+COUNTIFS('S5'!$B$6:$B$20,$A16,'S5'!$E$6:$E$20,"Diego")+COUNTIFS('S5'!$B$6:$B$20,$A16,'S5'!$E$6:$E$20,"Ambos")+COUNTIFS('S6'!$B$6:$B$17,$A16,'S6'!$E$6:$E$17,"Diego")+COUNTIFS('S6'!$B$6:$B$17,$A16,'S6'!$E$6:$E$17,"Ambos")+COUNTIFS('S7'!$B$6:$B$19,$A16,'S7'!$E$6:$E$19,"Diego")+COUNTIFS('S7'!$B$6:$B$19,$A16,'S7'!$E$6:$E$19,"Ambos")+COUNTIFS('S8'!$B$6:$B$23,$A16,'S8'!$E$6:$E$23,"Diego")+COUNTIFS('S8'!$B$6:$B$23,$A16,'S8'!$E$6:$E$23,"Ambos")+COUNTIFS('S9'!$B$6:$B$15,$A16,'S9'!$E$6:$E$15,"Diego")+COUNTIFS('S9'!$B$6:$B$15,$A16,'S9'!$E$6:$E$15,"Ambos")+COUNTIFS('S10'!$B$6:$B$13,$A16,'S10'!$E$6:$E$13,"Diego")+COUNTIFS('S10'!$B$6:$B$13,$A16,'S10'!$E$6:$E$13,"Ambos")+COUNTIFS('Holgura'!$B$6:$B$11,$A16,'Holgura'!$E$6:$E$11,"Diego")+COUNTIFS('Holgura'!$B$6:$B$11,$A16,'Holgura'!$E$6:$E$11,"Ambos")+COUNTIFS('Entrega'!$B$6:$B$9,$A16,'Entrega'!$E$6:$E$9,"Diego")+COUNTIFS('Entrega'!$B$6:$B$9,$A16,'Entrega'!$E$6:$E$9,"Ambos")+COUNTIFS('Defensa'!$B$6:$B$10,$A16,'Defensa'!$E$6:$E$10,"Diego")+COUNTIFS('Defensa'!$B$6:$B$10,$A16,'Defensa'!$E$6:$E$10,"Ambos")</f>
+        <f>COUNTIFS('S1'!$B$6:$B$32,$A16,'S1'!$E$6:$E$32,"Diego")+COUNTIFS('S1'!$B$6:$B$32,$A16,'S1'!$E$6:$E$32,"Ambos")+COUNTIFS('S2'!$B$6:$B$23,$A16,'S2'!$E$6:$E$23,"Diego")+COUNTIFS('S2'!$B$6:$B$23,$A16,'S2'!$E$6:$E$23,"Ambos")+COUNTIFS('S3'!$B$6:$B$24,$A16,'S3'!$E$6:$E$24,"Diego")+COUNTIFS('S3'!$B$6:$B$24,$A16,'S3'!$E$6:$E$24,"Ambos")+COUNTIFS('S4'!$B$6:$B$22,$A16,'S4'!$E$6:$E$22,"Diego")+COUNTIFS('S4'!$B$6:$B$22,$A16,'S4'!$E$6:$E$22,"Ambos")+COUNTIFS('S5'!$B$6:$B$20,$A16,'S5'!$E$6:$E$20,"Diego")+COUNTIFS('S5'!$B$6:$B$20,$A16,'S5'!$E$6:$E$20,"Ambos")+COUNTIFS('S6'!$B$6:$B$17,$A16,'S6'!$E$6:$E$17,"Diego")+COUNTIFS('S6'!$B$6:$B$17,$A16,'S6'!$E$6:$E$17,"Ambos")+COUNTIFS('S7'!$B$6:$B$19,$A16,'S7'!$E$6:$E$19,"Diego")+COUNTIFS('S7'!$B$6:$B$19,$A16,'S7'!$E$6:$E$19,"Ambos")+COUNTIFS('S8'!$B$6:$B$23,$A16,'S8'!$E$6:$E$23,"Diego")+COUNTIFS('S8'!$B$6:$B$23,$A16,'S8'!$E$6:$E$23,"Ambos")+COUNTIFS('S9'!$B$6:$B$15,$A16,'S9'!$E$6:$E$15,"Diego")+COUNTIFS('S9'!$B$6:$B$15,$A16,'S9'!$E$6:$E$15,"Ambos")+COUNTIFS('S10'!$B$6:$B$13,$A16,'S10'!$E$6:$E$13,"Diego")+COUNTIFS('S10'!$B$6:$B$13,$A16,'S10'!$E$6:$E$13,"Ambos")+COUNTIFS('Holgura'!$B$6:$B$11,$A16,'Holgura'!$E$6:$E$11,"Diego")+COUNTIFS('Holgura'!$B$6:$B$11,$A16,'Holgura'!$E$6:$E$11,"Ambos")+COUNTIFS('Entrega'!$B$6:$B$9,$A16,'Entrega'!$E$6:$E$9,"Diego")+COUNTIFS('Entrega'!$B$6:$B$9,$A16,'Entrega'!$E$6:$E$9,"Ambos")+COUNTIFS('Defensa'!$B$6:$B$10,$A16,'Defensa'!$E$6:$E$10,"Diego")+COUNTIFS('Defensa'!$B$6:$B$10,$A16,'Defensa'!$E$6:$E$10,"Ambos")</f>
         <v/>
       </c>
     </row>
@@ -9028,19 +9049,19 @@
         <v/>
       </c>
       <c r="D17" s="21">
-        <f>SUMIFS('S1'!$I$6:$I$32,'S1'!$B$6:$B$32,$A17,'S1'!$E$6:$E$32,"Víctor")+SUMIFS('S1'!$I$6:$I$32,'S1'!$B$6:$B$32,$A17,'S1'!$E$6:$E$32,"Ambos")+SUMIFS('S2'!$I$6:$I$23,'S2'!$B$6:$B$23,$A17,'S2'!$E$6:$E$23,"Víctor")+SUMIFS('S2'!$I$6:$I$23,'S2'!$B$6:$B$23,$A17,'S2'!$E$6:$E$23,"Ambos")+SUMIFS('S3'!$I$6:$I$19,'S3'!$B$6:$B$19,$A17,'S3'!$E$6:$E$19,"Víctor")+SUMIFS('S3'!$I$6:$I$19,'S3'!$B$6:$B$19,$A17,'S3'!$E$6:$E$19,"Ambos")+SUMIFS('S4'!$I$6:$I$20,'S4'!$B$6:$B$20,$A17,'S4'!$E$6:$E$20,"Víctor")+SUMIFS('S4'!$I$6:$I$20,'S4'!$B$6:$B$20,$A17,'S4'!$E$6:$E$20,"Ambos")+SUMIFS('S5'!$I$6:$I$20,'S5'!$B$6:$B$20,$A17,'S5'!$E$6:$E$20,"Víctor")+SUMIFS('S5'!$I$6:$I$20,'S5'!$B$6:$B$20,$A17,'S5'!$E$6:$E$20,"Ambos")+SUMIFS('S6'!$I$6:$I$17,'S6'!$B$6:$B$17,$A17,'S6'!$E$6:$E$17,"Víctor")+SUMIFS('S6'!$I$6:$I$17,'S6'!$B$6:$B$17,$A17,'S6'!$E$6:$E$17,"Ambos")+SUMIFS('S7'!$I$6:$I$19,'S7'!$B$6:$B$19,$A17,'S7'!$E$6:$E$19,"Víctor")+SUMIFS('S7'!$I$6:$I$19,'S7'!$B$6:$B$19,$A17,'S7'!$E$6:$E$19,"Ambos")+SUMIFS('S8'!$I$6:$I$23,'S8'!$B$6:$B$23,$A17,'S8'!$E$6:$E$23,"Víctor")+SUMIFS('S8'!$I$6:$I$23,'S8'!$B$6:$B$23,$A17,'S8'!$E$6:$E$23,"Ambos")+SUMIFS('S9'!$I$6:$I$15,'S9'!$B$6:$B$15,$A17,'S9'!$E$6:$E$15,"Víctor")+SUMIFS('S9'!$I$6:$I$15,'S9'!$B$6:$B$15,$A17,'S9'!$E$6:$E$15,"Ambos")+SUMIFS('S10'!$I$6:$I$13,'S10'!$B$6:$B$13,$A17,'S10'!$E$6:$E$13,"Víctor")+SUMIFS('S10'!$I$6:$I$13,'S10'!$B$6:$B$13,$A17,'S10'!$E$6:$E$13,"Ambos")+SUMIFS('Holgura'!$I$6:$I$11,'Holgura'!$B$6:$B$11,$A17,'Holgura'!$E$6:$E$11,"Víctor")+SUMIFS('Holgura'!$I$6:$I$11,'Holgura'!$B$6:$B$11,$A17,'Holgura'!$E$6:$E$11,"Ambos")+SUMIFS('Entrega'!$I$6:$I$9,'Entrega'!$B$6:$B$9,$A17,'Entrega'!$E$6:$E$9,"Víctor")+SUMIFS('Entrega'!$I$6:$I$9,'Entrega'!$B$6:$B$9,$A17,'Entrega'!$E$6:$E$9,"Ambos")+SUMIFS('Defensa'!$I$6:$I$10,'Defensa'!$B$6:$B$10,$A17,'Defensa'!$E$6:$E$10,"Víctor")+SUMIFS('Defensa'!$I$6:$I$10,'Defensa'!$B$6:$B$10,$A17,'Defensa'!$E$6:$E$10,"Ambos")</f>
+        <f>SUMIFS('S1'!$I$6:$I$32,'S1'!$B$6:$B$32,$A17,'S1'!$E$6:$E$32,"Víctor")+SUMIFS('S1'!$I$6:$I$32,'S1'!$B$6:$B$32,$A17,'S1'!$E$6:$E$32,"Ambos")+SUMIFS('S2'!$I$6:$I$23,'S2'!$B$6:$B$23,$A17,'S2'!$E$6:$E$23,"Víctor")+SUMIFS('S2'!$I$6:$I$23,'S2'!$B$6:$B$23,$A17,'S2'!$E$6:$E$23,"Ambos")+SUMIFS('S3'!$I$6:$I$24,'S3'!$B$6:$B$24,$A17,'S3'!$E$6:$E$24,"Víctor")+SUMIFS('S3'!$I$6:$I$24,'S3'!$B$6:$B$24,$A17,'S3'!$E$6:$E$24,"Ambos")+SUMIFS('S4'!$I$6:$I$22,'S4'!$B$6:$B$22,$A17,'S4'!$E$6:$E$22,"Víctor")+SUMIFS('S4'!$I$6:$I$22,'S4'!$B$6:$B$22,$A17,'S4'!$E$6:$E$22,"Ambos")+SUMIFS('S5'!$I$6:$I$20,'S5'!$B$6:$B$20,$A17,'S5'!$E$6:$E$20,"Víctor")+SUMIFS('S5'!$I$6:$I$20,'S5'!$B$6:$B$20,$A17,'S5'!$E$6:$E$20,"Ambos")+SUMIFS('S6'!$I$6:$I$17,'S6'!$B$6:$B$17,$A17,'S6'!$E$6:$E$17,"Víctor")+SUMIFS('S6'!$I$6:$I$17,'S6'!$B$6:$B$17,$A17,'S6'!$E$6:$E$17,"Ambos")+SUMIFS('S7'!$I$6:$I$19,'S7'!$B$6:$B$19,$A17,'S7'!$E$6:$E$19,"Víctor")+SUMIFS('S7'!$I$6:$I$19,'S7'!$B$6:$B$19,$A17,'S7'!$E$6:$E$19,"Ambos")+SUMIFS('S8'!$I$6:$I$23,'S8'!$B$6:$B$23,$A17,'S8'!$E$6:$E$23,"Víctor")+SUMIFS('S8'!$I$6:$I$23,'S8'!$B$6:$B$23,$A17,'S8'!$E$6:$E$23,"Ambos")+SUMIFS('S9'!$I$6:$I$15,'S9'!$B$6:$B$15,$A17,'S9'!$E$6:$E$15,"Víctor")+SUMIFS('S9'!$I$6:$I$15,'S9'!$B$6:$B$15,$A17,'S9'!$E$6:$E$15,"Ambos")+SUMIFS('S10'!$I$6:$I$13,'S10'!$B$6:$B$13,$A17,'S10'!$E$6:$E$13,"Víctor")+SUMIFS('S10'!$I$6:$I$13,'S10'!$B$6:$B$13,$A17,'S10'!$E$6:$E$13,"Ambos")+SUMIFS('Holgura'!$I$6:$I$11,'Holgura'!$B$6:$B$11,$A17,'Holgura'!$E$6:$E$11,"Víctor")+SUMIFS('Holgura'!$I$6:$I$11,'Holgura'!$B$6:$B$11,$A17,'Holgura'!$E$6:$E$11,"Ambos")+SUMIFS('Entrega'!$I$6:$I$9,'Entrega'!$B$6:$B$9,$A17,'Entrega'!$E$6:$E$9,"Víctor")+SUMIFS('Entrega'!$I$6:$I$9,'Entrega'!$B$6:$B$9,$A17,'Entrega'!$E$6:$E$9,"Ambos")+SUMIFS('Defensa'!$I$6:$I$10,'Defensa'!$B$6:$B$10,$A17,'Defensa'!$E$6:$E$10,"Víctor")+SUMIFS('Defensa'!$I$6:$I$10,'Defensa'!$B$6:$B$10,$A17,'Defensa'!$E$6:$E$10,"Ambos")</f>
         <v/>
       </c>
       <c r="E17" s="21">
-        <f>SUMIFS('S1'!$I$6:$I$32,'S1'!$B$6:$B$32,$A17,'S1'!$E$6:$E$32,"Diego")+SUMIFS('S1'!$I$6:$I$32,'S1'!$B$6:$B$32,$A17,'S1'!$E$6:$E$32,"Ambos")+SUMIFS('S2'!$I$6:$I$23,'S2'!$B$6:$B$23,$A17,'S2'!$E$6:$E$23,"Diego")+SUMIFS('S2'!$I$6:$I$23,'S2'!$B$6:$B$23,$A17,'S2'!$E$6:$E$23,"Ambos")+SUMIFS('S3'!$I$6:$I$19,'S3'!$B$6:$B$19,$A17,'S3'!$E$6:$E$19,"Diego")+SUMIFS('S3'!$I$6:$I$19,'S3'!$B$6:$B$19,$A17,'S3'!$E$6:$E$19,"Ambos")+SUMIFS('S4'!$I$6:$I$20,'S4'!$B$6:$B$20,$A17,'S4'!$E$6:$E$20,"Diego")+SUMIFS('S4'!$I$6:$I$20,'S4'!$B$6:$B$20,$A17,'S4'!$E$6:$E$20,"Ambos")+SUMIFS('S5'!$I$6:$I$20,'S5'!$B$6:$B$20,$A17,'S5'!$E$6:$E$20,"Diego")+SUMIFS('S5'!$I$6:$I$20,'S5'!$B$6:$B$20,$A17,'S5'!$E$6:$E$20,"Ambos")+SUMIFS('S6'!$I$6:$I$17,'S6'!$B$6:$B$17,$A17,'S6'!$E$6:$E$17,"Diego")+SUMIFS('S6'!$I$6:$I$17,'S6'!$B$6:$B$17,$A17,'S6'!$E$6:$E$17,"Ambos")+SUMIFS('S7'!$I$6:$I$19,'S7'!$B$6:$B$19,$A17,'S7'!$E$6:$E$19,"Diego")+SUMIFS('S7'!$I$6:$I$19,'S7'!$B$6:$B$19,$A17,'S7'!$E$6:$E$19,"Ambos")+SUMIFS('S8'!$I$6:$I$23,'S8'!$B$6:$B$23,$A17,'S8'!$E$6:$E$23,"Diego")+SUMIFS('S8'!$I$6:$I$23,'S8'!$B$6:$B$23,$A17,'S8'!$E$6:$E$23,"Ambos")+SUMIFS('S9'!$I$6:$I$15,'S9'!$B$6:$B$15,$A17,'S9'!$E$6:$E$15,"Diego")+SUMIFS('S9'!$I$6:$I$15,'S9'!$B$6:$B$15,$A17,'S9'!$E$6:$E$15,"Ambos")+SUMIFS('S10'!$I$6:$I$13,'S10'!$B$6:$B$13,$A17,'S10'!$E$6:$E$13,"Diego")+SUMIFS('S10'!$I$6:$I$13,'S10'!$B$6:$B$13,$A17,'S10'!$E$6:$E$13,"Ambos")+SUMIFS('Holgura'!$I$6:$I$11,'Holgura'!$B$6:$B$11,$A17,'Holgura'!$E$6:$E$11,"Diego")+SUMIFS('Holgura'!$I$6:$I$11,'Holgura'!$B$6:$B$11,$A17,'Holgura'!$E$6:$E$11,"Ambos")+SUMIFS('Entrega'!$I$6:$I$9,'Entrega'!$B$6:$B$9,$A17,'Entrega'!$E$6:$E$9,"Diego")+SUMIFS('Entrega'!$I$6:$I$9,'Entrega'!$B$6:$B$9,$A17,'Entrega'!$E$6:$E$9,"Ambos")+SUMIFS('Defensa'!$I$6:$I$10,'Defensa'!$B$6:$B$10,$A17,'Defensa'!$E$6:$E$10,"Diego")+SUMIFS('Defensa'!$I$6:$I$10,'Defensa'!$B$6:$B$10,$A17,'Defensa'!$E$6:$E$10,"Ambos")</f>
+        <f>SUMIFS('S1'!$I$6:$I$32,'S1'!$B$6:$B$32,$A17,'S1'!$E$6:$E$32,"Diego")+SUMIFS('S1'!$I$6:$I$32,'S1'!$B$6:$B$32,$A17,'S1'!$E$6:$E$32,"Ambos")+SUMIFS('S2'!$I$6:$I$23,'S2'!$B$6:$B$23,$A17,'S2'!$E$6:$E$23,"Diego")+SUMIFS('S2'!$I$6:$I$23,'S2'!$B$6:$B$23,$A17,'S2'!$E$6:$E$23,"Ambos")+SUMIFS('S3'!$I$6:$I$24,'S3'!$B$6:$B$24,$A17,'S3'!$E$6:$E$24,"Diego")+SUMIFS('S3'!$I$6:$I$24,'S3'!$B$6:$B$24,$A17,'S3'!$E$6:$E$24,"Ambos")+SUMIFS('S4'!$I$6:$I$22,'S4'!$B$6:$B$22,$A17,'S4'!$E$6:$E$22,"Diego")+SUMIFS('S4'!$I$6:$I$22,'S4'!$B$6:$B$22,$A17,'S4'!$E$6:$E$22,"Ambos")+SUMIFS('S5'!$I$6:$I$20,'S5'!$B$6:$B$20,$A17,'S5'!$E$6:$E$20,"Diego")+SUMIFS('S5'!$I$6:$I$20,'S5'!$B$6:$B$20,$A17,'S5'!$E$6:$E$20,"Ambos")+SUMIFS('S6'!$I$6:$I$17,'S6'!$B$6:$B$17,$A17,'S6'!$E$6:$E$17,"Diego")+SUMIFS('S6'!$I$6:$I$17,'S6'!$B$6:$B$17,$A17,'S6'!$E$6:$E$17,"Ambos")+SUMIFS('S7'!$I$6:$I$19,'S7'!$B$6:$B$19,$A17,'S7'!$E$6:$E$19,"Diego")+SUMIFS('S7'!$I$6:$I$19,'S7'!$B$6:$B$19,$A17,'S7'!$E$6:$E$19,"Ambos")+SUMIFS('S8'!$I$6:$I$23,'S8'!$B$6:$B$23,$A17,'S8'!$E$6:$E$23,"Diego")+SUMIFS('S8'!$I$6:$I$23,'S8'!$B$6:$B$23,$A17,'S8'!$E$6:$E$23,"Ambos")+SUMIFS('S9'!$I$6:$I$15,'S9'!$B$6:$B$15,$A17,'S9'!$E$6:$E$15,"Diego")+SUMIFS('S9'!$I$6:$I$15,'S9'!$B$6:$B$15,$A17,'S9'!$E$6:$E$15,"Ambos")+SUMIFS('S10'!$I$6:$I$13,'S10'!$B$6:$B$13,$A17,'S10'!$E$6:$E$13,"Diego")+SUMIFS('S10'!$I$6:$I$13,'S10'!$B$6:$B$13,$A17,'S10'!$E$6:$E$13,"Ambos")+SUMIFS('Holgura'!$I$6:$I$11,'Holgura'!$B$6:$B$11,$A17,'Holgura'!$E$6:$E$11,"Diego")+SUMIFS('Holgura'!$I$6:$I$11,'Holgura'!$B$6:$B$11,$A17,'Holgura'!$E$6:$E$11,"Ambos")+SUMIFS('Entrega'!$I$6:$I$9,'Entrega'!$B$6:$B$9,$A17,'Entrega'!$E$6:$E$9,"Diego")+SUMIFS('Entrega'!$I$6:$I$9,'Entrega'!$B$6:$B$9,$A17,'Entrega'!$E$6:$E$9,"Ambos")+SUMIFS('Defensa'!$I$6:$I$10,'Defensa'!$B$6:$B$10,$A17,'Defensa'!$E$6:$E$10,"Diego")+SUMIFS('Defensa'!$I$6:$I$10,'Defensa'!$B$6:$B$10,$A17,'Defensa'!$E$6:$E$10,"Ambos")</f>
         <v/>
       </c>
       <c r="F17" s="21">
-        <f>COUNTIFS('S1'!$B$6:$B$32,$A17,'S1'!$E$6:$E$32,"Víctor")+COUNTIFS('S1'!$B$6:$B$32,$A17,'S1'!$E$6:$E$32,"Ambos")+COUNTIFS('S2'!$B$6:$B$23,$A17,'S2'!$E$6:$E$23,"Víctor")+COUNTIFS('S2'!$B$6:$B$23,$A17,'S2'!$E$6:$E$23,"Ambos")+COUNTIFS('S3'!$B$6:$B$19,$A17,'S3'!$E$6:$E$19,"Víctor")+COUNTIFS('S3'!$B$6:$B$19,$A17,'S3'!$E$6:$E$19,"Ambos")+COUNTIFS('S4'!$B$6:$B$20,$A17,'S4'!$E$6:$E$20,"Víctor")+COUNTIFS('S4'!$B$6:$B$20,$A17,'S4'!$E$6:$E$20,"Ambos")+COUNTIFS('S5'!$B$6:$B$20,$A17,'S5'!$E$6:$E$20,"Víctor")+COUNTIFS('S5'!$B$6:$B$20,$A17,'S5'!$E$6:$E$20,"Ambos")+COUNTIFS('S6'!$B$6:$B$17,$A17,'S6'!$E$6:$E$17,"Víctor")+COUNTIFS('S6'!$B$6:$B$17,$A17,'S6'!$E$6:$E$17,"Ambos")+COUNTIFS('S7'!$B$6:$B$19,$A17,'S7'!$E$6:$E$19,"Víctor")+COUNTIFS('S7'!$B$6:$B$19,$A17,'S7'!$E$6:$E$19,"Ambos")+COUNTIFS('S8'!$B$6:$B$23,$A17,'S8'!$E$6:$E$23,"Víctor")+COUNTIFS('S8'!$B$6:$B$23,$A17,'S8'!$E$6:$E$23,"Ambos")+COUNTIFS('S9'!$B$6:$B$15,$A17,'S9'!$E$6:$E$15,"Víctor")+COUNTIFS('S9'!$B$6:$B$15,$A17,'S9'!$E$6:$E$15,"Ambos")+COUNTIFS('S10'!$B$6:$B$13,$A17,'S10'!$E$6:$E$13,"Víctor")+COUNTIFS('S10'!$B$6:$B$13,$A17,'S10'!$E$6:$E$13,"Ambos")+COUNTIFS('Holgura'!$B$6:$B$11,$A17,'Holgura'!$E$6:$E$11,"Víctor")+COUNTIFS('Holgura'!$B$6:$B$11,$A17,'Holgura'!$E$6:$E$11,"Ambos")+COUNTIFS('Entrega'!$B$6:$B$9,$A17,'Entrega'!$E$6:$E$9,"Víctor")+COUNTIFS('Entrega'!$B$6:$B$9,$A17,'Entrega'!$E$6:$E$9,"Ambos")+COUNTIFS('Defensa'!$B$6:$B$10,$A17,'Defensa'!$E$6:$E$10,"Víctor")+COUNTIFS('Defensa'!$B$6:$B$10,$A17,'Defensa'!$E$6:$E$10,"Ambos")</f>
+        <f>COUNTIFS('S1'!$B$6:$B$32,$A17,'S1'!$E$6:$E$32,"Víctor")+COUNTIFS('S1'!$B$6:$B$32,$A17,'S1'!$E$6:$E$32,"Ambos")+COUNTIFS('S2'!$B$6:$B$23,$A17,'S2'!$E$6:$E$23,"Víctor")+COUNTIFS('S2'!$B$6:$B$23,$A17,'S2'!$E$6:$E$23,"Ambos")+COUNTIFS('S3'!$B$6:$B$24,$A17,'S3'!$E$6:$E$24,"Víctor")+COUNTIFS('S3'!$B$6:$B$24,$A17,'S3'!$E$6:$E$24,"Ambos")+COUNTIFS('S4'!$B$6:$B$22,$A17,'S4'!$E$6:$E$22,"Víctor")+COUNTIFS('S4'!$B$6:$B$22,$A17,'S4'!$E$6:$E$22,"Ambos")+COUNTIFS('S5'!$B$6:$B$20,$A17,'S5'!$E$6:$E$20,"Víctor")+COUNTIFS('S5'!$B$6:$B$20,$A17,'S5'!$E$6:$E$20,"Ambos")+COUNTIFS('S6'!$B$6:$B$17,$A17,'S6'!$E$6:$E$17,"Víctor")+COUNTIFS('S6'!$B$6:$B$17,$A17,'S6'!$E$6:$E$17,"Ambos")+COUNTIFS('S7'!$B$6:$B$19,$A17,'S7'!$E$6:$E$19,"Víctor")+COUNTIFS('S7'!$B$6:$B$19,$A17,'S7'!$E$6:$E$19,"Ambos")+COUNTIFS('S8'!$B$6:$B$23,$A17,'S8'!$E$6:$E$23,"Víctor")+COUNTIFS('S8'!$B$6:$B$23,$A17,'S8'!$E$6:$E$23,"Ambos")+COUNTIFS('S9'!$B$6:$B$15,$A17,'S9'!$E$6:$E$15,"Víctor")+COUNTIFS('S9'!$B$6:$B$15,$A17,'S9'!$E$6:$E$15,"Ambos")+COUNTIFS('S10'!$B$6:$B$13,$A17,'S10'!$E$6:$E$13,"Víctor")+COUNTIFS('S10'!$B$6:$B$13,$A17,'S10'!$E$6:$E$13,"Ambos")+COUNTIFS('Holgura'!$B$6:$B$11,$A17,'Holgura'!$E$6:$E$11,"Víctor")+COUNTIFS('Holgura'!$B$6:$B$11,$A17,'Holgura'!$E$6:$E$11,"Ambos")+COUNTIFS('Entrega'!$B$6:$B$9,$A17,'Entrega'!$E$6:$E$9,"Víctor")+COUNTIFS('Entrega'!$B$6:$B$9,$A17,'Entrega'!$E$6:$E$9,"Ambos")+COUNTIFS('Defensa'!$B$6:$B$10,$A17,'Defensa'!$E$6:$E$10,"Víctor")+COUNTIFS('Defensa'!$B$6:$B$10,$A17,'Defensa'!$E$6:$E$10,"Ambos")</f>
         <v/>
       </c>
       <c r="G17" s="21">
-        <f>COUNTIFS('S1'!$B$6:$B$32,$A17,'S1'!$E$6:$E$32,"Diego")+COUNTIFS('S1'!$B$6:$B$32,$A17,'S1'!$E$6:$E$32,"Ambos")+COUNTIFS('S2'!$B$6:$B$23,$A17,'S2'!$E$6:$E$23,"Diego")+COUNTIFS('S2'!$B$6:$B$23,$A17,'S2'!$E$6:$E$23,"Ambos")+COUNTIFS('S3'!$B$6:$B$19,$A17,'S3'!$E$6:$E$19,"Diego")+COUNTIFS('S3'!$B$6:$B$19,$A17,'S3'!$E$6:$E$19,"Ambos")+COUNTIFS('S4'!$B$6:$B$20,$A17,'S4'!$E$6:$E$20,"Diego")+COUNTIFS('S4'!$B$6:$B$20,$A17,'S4'!$E$6:$E$20,"Ambos")+COUNTIFS('S5'!$B$6:$B$20,$A17,'S5'!$E$6:$E$20,"Diego")+COUNTIFS('S5'!$B$6:$B$20,$A17,'S5'!$E$6:$E$20,"Ambos")+COUNTIFS('S6'!$B$6:$B$17,$A17,'S6'!$E$6:$E$17,"Diego")+COUNTIFS('S6'!$B$6:$B$17,$A17,'S6'!$E$6:$E$17,"Ambos")+COUNTIFS('S7'!$B$6:$B$19,$A17,'S7'!$E$6:$E$19,"Diego")+COUNTIFS('S7'!$B$6:$B$19,$A17,'S7'!$E$6:$E$19,"Ambos")+COUNTIFS('S8'!$B$6:$B$23,$A17,'S8'!$E$6:$E$23,"Diego")+COUNTIFS('S8'!$B$6:$B$23,$A17,'S8'!$E$6:$E$23,"Ambos")+COUNTIFS('S9'!$B$6:$B$15,$A17,'S9'!$E$6:$E$15,"Diego")+COUNTIFS('S9'!$B$6:$B$15,$A17,'S9'!$E$6:$E$15,"Ambos")+COUNTIFS('S10'!$B$6:$B$13,$A17,'S10'!$E$6:$E$13,"Diego")+COUNTIFS('S10'!$B$6:$B$13,$A17,'S10'!$E$6:$E$13,"Ambos")+COUNTIFS('Holgura'!$B$6:$B$11,$A17,'Holgura'!$E$6:$E$11,"Diego")+COUNTIFS('Holgura'!$B$6:$B$11,$A17,'Holgura'!$E$6:$E$11,"Ambos")+COUNTIFS('Entrega'!$B$6:$B$9,$A17,'Entrega'!$E$6:$E$9,"Diego")+COUNTIFS('Entrega'!$B$6:$B$9,$A17,'Entrega'!$E$6:$E$9,"Ambos")+COUNTIFS('Defensa'!$B$6:$B$10,$A17,'Defensa'!$E$6:$E$10,"Diego")+COUNTIFS('Defensa'!$B$6:$B$10,$A17,'Defensa'!$E$6:$E$10,"Ambos")</f>
+        <f>COUNTIFS('S1'!$B$6:$B$32,$A17,'S1'!$E$6:$E$32,"Diego")+COUNTIFS('S1'!$B$6:$B$32,$A17,'S1'!$E$6:$E$32,"Ambos")+COUNTIFS('S2'!$B$6:$B$23,$A17,'S2'!$E$6:$E$23,"Diego")+COUNTIFS('S2'!$B$6:$B$23,$A17,'S2'!$E$6:$E$23,"Ambos")+COUNTIFS('S3'!$B$6:$B$24,$A17,'S3'!$E$6:$E$24,"Diego")+COUNTIFS('S3'!$B$6:$B$24,$A17,'S3'!$E$6:$E$24,"Ambos")+COUNTIFS('S4'!$B$6:$B$22,$A17,'S4'!$E$6:$E$22,"Diego")+COUNTIFS('S4'!$B$6:$B$22,$A17,'S4'!$E$6:$E$22,"Ambos")+COUNTIFS('S5'!$B$6:$B$20,$A17,'S5'!$E$6:$E$20,"Diego")+COUNTIFS('S5'!$B$6:$B$20,$A17,'S5'!$E$6:$E$20,"Ambos")+COUNTIFS('S6'!$B$6:$B$17,$A17,'S6'!$E$6:$E$17,"Diego")+COUNTIFS('S6'!$B$6:$B$17,$A17,'S6'!$E$6:$E$17,"Ambos")+COUNTIFS('S7'!$B$6:$B$19,$A17,'S7'!$E$6:$E$19,"Diego")+COUNTIFS('S7'!$B$6:$B$19,$A17,'S7'!$E$6:$E$19,"Ambos")+COUNTIFS('S8'!$B$6:$B$23,$A17,'S8'!$E$6:$E$23,"Diego")+COUNTIFS('S8'!$B$6:$B$23,$A17,'S8'!$E$6:$E$23,"Ambos")+COUNTIFS('S9'!$B$6:$B$15,$A17,'S9'!$E$6:$E$15,"Diego")+COUNTIFS('S9'!$B$6:$B$15,$A17,'S9'!$E$6:$E$15,"Ambos")+COUNTIFS('S10'!$B$6:$B$13,$A17,'S10'!$E$6:$E$13,"Diego")+COUNTIFS('S10'!$B$6:$B$13,$A17,'S10'!$E$6:$E$13,"Ambos")+COUNTIFS('Holgura'!$B$6:$B$11,$A17,'Holgura'!$E$6:$E$11,"Diego")+COUNTIFS('Holgura'!$B$6:$B$11,$A17,'Holgura'!$E$6:$E$11,"Ambos")+COUNTIFS('Entrega'!$B$6:$B$9,$A17,'Entrega'!$E$6:$E$9,"Diego")+COUNTIFS('Entrega'!$B$6:$B$9,$A17,'Entrega'!$E$6:$E$9,"Ambos")+COUNTIFS('Defensa'!$B$6:$B$10,$A17,'Defensa'!$E$6:$E$10,"Diego")+COUNTIFS('Defensa'!$B$6:$B$10,$A17,'Defensa'!$E$6:$E$10,"Ambos")</f>
         <v/>
       </c>
     </row>
@@ -9057,19 +9078,19 @@
         <v/>
       </c>
       <c r="D18" s="21">
-        <f>SUMIFS('S1'!$I$6:$I$32,'S1'!$B$6:$B$32,$A18,'S1'!$E$6:$E$32,"Víctor")+SUMIFS('S1'!$I$6:$I$32,'S1'!$B$6:$B$32,$A18,'S1'!$E$6:$E$32,"Ambos")+SUMIFS('S2'!$I$6:$I$23,'S2'!$B$6:$B$23,$A18,'S2'!$E$6:$E$23,"Víctor")+SUMIFS('S2'!$I$6:$I$23,'S2'!$B$6:$B$23,$A18,'S2'!$E$6:$E$23,"Ambos")+SUMIFS('S3'!$I$6:$I$19,'S3'!$B$6:$B$19,$A18,'S3'!$E$6:$E$19,"Víctor")+SUMIFS('S3'!$I$6:$I$19,'S3'!$B$6:$B$19,$A18,'S3'!$E$6:$E$19,"Ambos")+SUMIFS('S4'!$I$6:$I$20,'S4'!$B$6:$B$20,$A18,'S4'!$E$6:$E$20,"Víctor")+SUMIFS('S4'!$I$6:$I$20,'S4'!$B$6:$B$20,$A18,'S4'!$E$6:$E$20,"Ambos")+SUMIFS('S5'!$I$6:$I$20,'S5'!$B$6:$B$20,$A18,'S5'!$E$6:$E$20,"Víctor")+SUMIFS('S5'!$I$6:$I$20,'S5'!$B$6:$B$20,$A18,'S5'!$E$6:$E$20,"Ambos")+SUMIFS('S6'!$I$6:$I$17,'S6'!$B$6:$B$17,$A18,'S6'!$E$6:$E$17,"Víctor")+SUMIFS('S6'!$I$6:$I$17,'S6'!$B$6:$B$17,$A18,'S6'!$E$6:$E$17,"Ambos")+SUMIFS('S7'!$I$6:$I$19,'S7'!$B$6:$B$19,$A18,'S7'!$E$6:$E$19,"Víctor")+SUMIFS('S7'!$I$6:$I$19,'S7'!$B$6:$B$19,$A18,'S7'!$E$6:$E$19,"Ambos")+SUMIFS('S8'!$I$6:$I$23,'S8'!$B$6:$B$23,$A18,'S8'!$E$6:$E$23,"Víctor")+SUMIFS('S8'!$I$6:$I$23,'S8'!$B$6:$B$23,$A18,'S8'!$E$6:$E$23,"Ambos")+SUMIFS('S9'!$I$6:$I$15,'S9'!$B$6:$B$15,$A18,'S9'!$E$6:$E$15,"Víctor")+SUMIFS('S9'!$I$6:$I$15,'S9'!$B$6:$B$15,$A18,'S9'!$E$6:$E$15,"Ambos")+SUMIFS('S10'!$I$6:$I$13,'S10'!$B$6:$B$13,$A18,'S10'!$E$6:$E$13,"Víctor")+SUMIFS('S10'!$I$6:$I$13,'S10'!$B$6:$B$13,$A18,'S10'!$E$6:$E$13,"Ambos")+SUMIFS('Holgura'!$I$6:$I$11,'Holgura'!$B$6:$B$11,$A18,'Holgura'!$E$6:$E$11,"Víctor")+SUMIFS('Holgura'!$I$6:$I$11,'Holgura'!$B$6:$B$11,$A18,'Holgura'!$E$6:$E$11,"Ambos")+SUMIFS('Entrega'!$I$6:$I$9,'Entrega'!$B$6:$B$9,$A18,'Entrega'!$E$6:$E$9,"Víctor")+SUMIFS('Entrega'!$I$6:$I$9,'Entrega'!$B$6:$B$9,$A18,'Entrega'!$E$6:$E$9,"Ambos")+SUMIFS('Defensa'!$I$6:$I$10,'Defensa'!$B$6:$B$10,$A18,'Defensa'!$E$6:$E$10,"Víctor")+SUMIFS('Defensa'!$I$6:$I$10,'Defensa'!$B$6:$B$10,$A18,'Defensa'!$E$6:$E$10,"Ambos")</f>
+        <f>SUMIFS('S1'!$I$6:$I$32,'S1'!$B$6:$B$32,$A18,'S1'!$E$6:$E$32,"Víctor")+SUMIFS('S1'!$I$6:$I$32,'S1'!$B$6:$B$32,$A18,'S1'!$E$6:$E$32,"Ambos")+SUMIFS('S2'!$I$6:$I$23,'S2'!$B$6:$B$23,$A18,'S2'!$E$6:$E$23,"Víctor")+SUMIFS('S2'!$I$6:$I$23,'S2'!$B$6:$B$23,$A18,'S2'!$E$6:$E$23,"Ambos")+SUMIFS('S3'!$I$6:$I$24,'S3'!$B$6:$B$24,$A18,'S3'!$E$6:$E$24,"Víctor")+SUMIFS('S3'!$I$6:$I$24,'S3'!$B$6:$B$24,$A18,'S3'!$E$6:$E$24,"Ambos")+SUMIFS('S4'!$I$6:$I$22,'S4'!$B$6:$B$22,$A18,'S4'!$E$6:$E$22,"Víctor")+SUMIFS('S4'!$I$6:$I$22,'S4'!$B$6:$B$22,$A18,'S4'!$E$6:$E$22,"Ambos")+SUMIFS('S5'!$I$6:$I$20,'S5'!$B$6:$B$20,$A18,'S5'!$E$6:$E$20,"Víctor")+SUMIFS('S5'!$I$6:$I$20,'S5'!$B$6:$B$20,$A18,'S5'!$E$6:$E$20,"Ambos")+SUMIFS('S6'!$I$6:$I$17,'S6'!$B$6:$B$17,$A18,'S6'!$E$6:$E$17,"Víctor")+SUMIFS('S6'!$I$6:$I$17,'S6'!$B$6:$B$17,$A18,'S6'!$E$6:$E$17,"Ambos")+SUMIFS('S7'!$I$6:$I$19,'S7'!$B$6:$B$19,$A18,'S7'!$E$6:$E$19,"Víctor")+SUMIFS('S7'!$I$6:$I$19,'S7'!$B$6:$B$19,$A18,'S7'!$E$6:$E$19,"Ambos")+SUMIFS('S8'!$I$6:$I$23,'S8'!$B$6:$B$23,$A18,'S8'!$E$6:$E$23,"Víctor")+SUMIFS('S8'!$I$6:$I$23,'S8'!$B$6:$B$23,$A18,'S8'!$E$6:$E$23,"Ambos")+SUMIFS('S9'!$I$6:$I$15,'S9'!$B$6:$B$15,$A18,'S9'!$E$6:$E$15,"Víctor")+SUMIFS('S9'!$I$6:$I$15,'S9'!$B$6:$B$15,$A18,'S9'!$E$6:$E$15,"Ambos")+SUMIFS('S10'!$I$6:$I$13,'S10'!$B$6:$B$13,$A18,'S10'!$E$6:$E$13,"Víctor")+SUMIFS('S10'!$I$6:$I$13,'S10'!$B$6:$B$13,$A18,'S10'!$E$6:$E$13,"Ambos")+SUMIFS('Holgura'!$I$6:$I$11,'Holgura'!$B$6:$B$11,$A18,'Holgura'!$E$6:$E$11,"Víctor")+SUMIFS('Holgura'!$I$6:$I$11,'Holgura'!$B$6:$B$11,$A18,'Holgura'!$E$6:$E$11,"Ambos")+SUMIFS('Entrega'!$I$6:$I$9,'Entrega'!$B$6:$B$9,$A18,'Entrega'!$E$6:$E$9,"Víctor")+SUMIFS('Entrega'!$I$6:$I$9,'Entrega'!$B$6:$B$9,$A18,'Entrega'!$E$6:$E$9,"Ambos")+SUMIFS('Defensa'!$I$6:$I$10,'Defensa'!$B$6:$B$10,$A18,'Defensa'!$E$6:$E$10,"Víctor")+SUMIFS('Defensa'!$I$6:$I$10,'Defensa'!$B$6:$B$10,$A18,'Defensa'!$E$6:$E$10,"Ambos")</f>
         <v/>
       </c>
       <c r="E18" s="21">
-        <f>SUMIFS('S1'!$I$6:$I$32,'S1'!$B$6:$B$32,$A18,'S1'!$E$6:$E$32,"Diego")+SUMIFS('S1'!$I$6:$I$32,'S1'!$B$6:$B$32,$A18,'S1'!$E$6:$E$32,"Ambos")+SUMIFS('S2'!$I$6:$I$23,'S2'!$B$6:$B$23,$A18,'S2'!$E$6:$E$23,"Diego")+SUMIFS('S2'!$I$6:$I$23,'S2'!$B$6:$B$23,$A18,'S2'!$E$6:$E$23,"Ambos")+SUMIFS('S3'!$I$6:$I$19,'S3'!$B$6:$B$19,$A18,'S3'!$E$6:$E$19,"Diego")+SUMIFS('S3'!$I$6:$I$19,'S3'!$B$6:$B$19,$A18,'S3'!$E$6:$E$19,"Ambos")+SUMIFS('S4'!$I$6:$I$20,'S4'!$B$6:$B$20,$A18,'S4'!$E$6:$E$20,"Diego")+SUMIFS('S4'!$I$6:$I$20,'S4'!$B$6:$B$20,$A18,'S4'!$E$6:$E$20,"Ambos")+SUMIFS('S5'!$I$6:$I$20,'S5'!$B$6:$B$20,$A18,'S5'!$E$6:$E$20,"Diego")+SUMIFS('S5'!$I$6:$I$20,'S5'!$B$6:$B$20,$A18,'S5'!$E$6:$E$20,"Ambos")+SUMIFS('S6'!$I$6:$I$17,'S6'!$B$6:$B$17,$A18,'S6'!$E$6:$E$17,"Diego")+SUMIFS('S6'!$I$6:$I$17,'S6'!$B$6:$B$17,$A18,'S6'!$E$6:$E$17,"Ambos")+SUMIFS('S7'!$I$6:$I$19,'S7'!$B$6:$B$19,$A18,'S7'!$E$6:$E$19,"Diego")+SUMIFS('S7'!$I$6:$I$19,'S7'!$B$6:$B$19,$A18,'S7'!$E$6:$E$19,"Ambos")+SUMIFS('S8'!$I$6:$I$23,'S8'!$B$6:$B$23,$A18,'S8'!$E$6:$E$23,"Diego")+SUMIFS('S8'!$I$6:$I$23,'S8'!$B$6:$B$23,$A18,'S8'!$E$6:$E$23,"Ambos")+SUMIFS('S9'!$I$6:$I$15,'S9'!$B$6:$B$15,$A18,'S9'!$E$6:$E$15,"Diego")+SUMIFS('S9'!$I$6:$I$15,'S9'!$B$6:$B$15,$A18,'S9'!$E$6:$E$15,"Ambos")+SUMIFS('S10'!$I$6:$I$13,'S10'!$B$6:$B$13,$A18,'S10'!$E$6:$E$13,"Diego")+SUMIFS('S10'!$I$6:$I$13,'S10'!$B$6:$B$13,$A18,'S10'!$E$6:$E$13,"Ambos")+SUMIFS('Holgura'!$I$6:$I$11,'Holgura'!$B$6:$B$11,$A18,'Holgura'!$E$6:$E$11,"Diego")+SUMIFS('Holgura'!$I$6:$I$11,'Holgura'!$B$6:$B$11,$A18,'Holgura'!$E$6:$E$11,"Ambos")+SUMIFS('Entrega'!$I$6:$I$9,'Entrega'!$B$6:$B$9,$A18,'Entrega'!$E$6:$E$9,"Diego")+SUMIFS('Entrega'!$I$6:$I$9,'Entrega'!$B$6:$B$9,$A18,'Entrega'!$E$6:$E$9,"Ambos")+SUMIFS('Defensa'!$I$6:$I$10,'Defensa'!$B$6:$B$10,$A18,'Defensa'!$E$6:$E$10,"Diego")+SUMIFS('Defensa'!$I$6:$I$10,'Defensa'!$B$6:$B$10,$A18,'Defensa'!$E$6:$E$10,"Ambos")</f>
+        <f>SUMIFS('S1'!$I$6:$I$32,'S1'!$B$6:$B$32,$A18,'S1'!$E$6:$E$32,"Diego")+SUMIFS('S1'!$I$6:$I$32,'S1'!$B$6:$B$32,$A18,'S1'!$E$6:$E$32,"Ambos")+SUMIFS('S2'!$I$6:$I$23,'S2'!$B$6:$B$23,$A18,'S2'!$E$6:$E$23,"Diego")+SUMIFS('S2'!$I$6:$I$23,'S2'!$B$6:$B$23,$A18,'S2'!$E$6:$E$23,"Ambos")+SUMIFS('S3'!$I$6:$I$24,'S3'!$B$6:$B$24,$A18,'S3'!$E$6:$E$24,"Diego")+SUMIFS('S3'!$I$6:$I$24,'S3'!$B$6:$B$24,$A18,'S3'!$E$6:$E$24,"Ambos")+SUMIFS('S4'!$I$6:$I$22,'S4'!$B$6:$B$22,$A18,'S4'!$E$6:$E$22,"Diego")+SUMIFS('S4'!$I$6:$I$22,'S4'!$B$6:$B$22,$A18,'S4'!$E$6:$E$22,"Ambos")+SUMIFS('S5'!$I$6:$I$20,'S5'!$B$6:$B$20,$A18,'S5'!$E$6:$E$20,"Diego")+SUMIFS('S5'!$I$6:$I$20,'S5'!$B$6:$B$20,$A18,'S5'!$E$6:$E$20,"Ambos")+SUMIFS('S6'!$I$6:$I$17,'S6'!$B$6:$B$17,$A18,'S6'!$E$6:$E$17,"Diego")+SUMIFS('S6'!$I$6:$I$17,'S6'!$B$6:$B$17,$A18,'S6'!$E$6:$E$17,"Ambos")+SUMIFS('S7'!$I$6:$I$19,'S7'!$B$6:$B$19,$A18,'S7'!$E$6:$E$19,"Diego")+SUMIFS('S7'!$I$6:$I$19,'S7'!$B$6:$B$19,$A18,'S7'!$E$6:$E$19,"Ambos")+SUMIFS('S8'!$I$6:$I$23,'S8'!$B$6:$B$23,$A18,'S8'!$E$6:$E$23,"Diego")+SUMIFS('S8'!$I$6:$I$23,'S8'!$B$6:$B$23,$A18,'S8'!$E$6:$E$23,"Ambos")+SUMIFS('S9'!$I$6:$I$15,'S9'!$B$6:$B$15,$A18,'S9'!$E$6:$E$15,"Diego")+SUMIFS('S9'!$I$6:$I$15,'S9'!$B$6:$B$15,$A18,'S9'!$E$6:$E$15,"Ambos")+SUMIFS('S10'!$I$6:$I$13,'S10'!$B$6:$B$13,$A18,'S10'!$E$6:$E$13,"Diego")+SUMIFS('S10'!$I$6:$I$13,'S10'!$B$6:$B$13,$A18,'S10'!$E$6:$E$13,"Ambos")+SUMIFS('Holgura'!$I$6:$I$11,'Holgura'!$B$6:$B$11,$A18,'Holgura'!$E$6:$E$11,"Diego")+SUMIFS('Holgura'!$I$6:$I$11,'Holgura'!$B$6:$B$11,$A18,'Holgura'!$E$6:$E$11,"Ambos")+SUMIFS('Entrega'!$I$6:$I$9,'Entrega'!$B$6:$B$9,$A18,'Entrega'!$E$6:$E$9,"Diego")+SUMIFS('Entrega'!$I$6:$I$9,'Entrega'!$B$6:$B$9,$A18,'Entrega'!$E$6:$E$9,"Ambos")+SUMIFS('Defensa'!$I$6:$I$10,'Defensa'!$B$6:$B$10,$A18,'Defensa'!$E$6:$E$10,"Diego")+SUMIFS('Defensa'!$I$6:$I$10,'Defensa'!$B$6:$B$10,$A18,'Defensa'!$E$6:$E$10,"Ambos")</f>
         <v/>
       </c>
       <c r="F18" s="21">
-        <f>COUNTIFS('S1'!$B$6:$B$32,$A18,'S1'!$E$6:$E$32,"Víctor")+COUNTIFS('S1'!$B$6:$B$32,$A18,'S1'!$E$6:$E$32,"Ambos")+COUNTIFS('S2'!$B$6:$B$23,$A18,'S2'!$E$6:$E$23,"Víctor")+COUNTIFS('S2'!$B$6:$B$23,$A18,'S2'!$E$6:$E$23,"Ambos")+COUNTIFS('S3'!$B$6:$B$19,$A18,'S3'!$E$6:$E$19,"Víctor")+COUNTIFS('S3'!$B$6:$B$19,$A18,'S3'!$E$6:$E$19,"Ambos")+COUNTIFS('S4'!$B$6:$B$20,$A18,'S4'!$E$6:$E$20,"Víctor")+COUNTIFS('S4'!$B$6:$B$20,$A18,'S4'!$E$6:$E$20,"Ambos")+COUNTIFS('S5'!$B$6:$B$20,$A18,'S5'!$E$6:$E$20,"Víctor")+COUNTIFS('S5'!$B$6:$B$20,$A18,'S5'!$E$6:$E$20,"Ambos")+COUNTIFS('S6'!$B$6:$B$17,$A18,'S6'!$E$6:$E$17,"Víctor")+COUNTIFS('S6'!$B$6:$B$17,$A18,'S6'!$E$6:$E$17,"Ambos")+COUNTIFS('S7'!$B$6:$B$19,$A18,'S7'!$E$6:$E$19,"Víctor")+COUNTIFS('S7'!$B$6:$B$19,$A18,'S7'!$E$6:$E$19,"Ambos")+COUNTIFS('S8'!$B$6:$B$23,$A18,'S8'!$E$6:$E$23,"Víctor")+COUNTIFS('S8'!$B$6:$B$23,$A18,'S8'!$E$6:$E$23,"Ambos")+COUNTIFS('S9'!$B$6:$B$15,$A18,'S9'!$E$6:$E$15,"Víctor")+COUNTIFS('S9'!$B$6:$B$15,$A18,'S9'!$E$6:$E$15,"Ambos")+COUNTIFS('S10'!$B$6:$B$13,$A18,'S10'!$E$6:$E$13,"Víctor")+COUNTIFS('S10'!$B$6:$B$13,$A18,'S10'!$E$6:$E$13,"Ambos")+COUNTIFS('Holgura'!$B$6:$B$11,$A18,'Holgura'!$E$6:$E$11,"Víctor")+COUNTIFS('Holgura'!$B$6:$B$11,$A18,'Holgura'!$E$6:$E$11,"Ambos")+COUNTIFS('Entrega'!$B$6:$B$9,$A18,'Entrega'!$E$6:$E$9,"Víctor")+COUNTIFS('Entrega'!$B$6:$B$9,$A18,'Entrega'!$E$6:$E$9,"Ambos")+COUNTIFS('Defensa'!$B$6:$B$10,$A18,'Defensa'!$E$6:$E$10,"Víctor")+COUNTIFS('Defensa'!$B$6:$B$10,$A18,'Defensa'!$E$6:$E$10,"Ambos")</f>
+        <f>COUNTIFS('S1'!$B$6:$B$32,$A18,'S1'!$E$6:$E$32,"Víctor")+COUNTIFS('S1'!$B$6:$B$32,$A18,'S1'!$E$6:$E$32,"Ambos")+COUNTIFS('S2'!$B$6:$B$23,$A18,'S2'!$E$6:$E$23,"Víctor")+COUNTIFS('S2'!$B$6:$B$23,$A18,'S2'!$E$6:$E$23,"Ambos")+COUNTIFS('S3'!$B$6:$B$24,$A18,'S3'!$E$6:$E$24,"Víctor")+COUNTIFS('S3'!$B$6:$B$24,$A18,'S3'!$E$6:$E$24,"Ambos")+COUNTIFS('S4'!$B$6:$B$22,$A18,'S4'!$E$6:$E$22,"Víctor")+COUNTIFS('S4'!$B$6:$B$22,$A18,'S4'!$E$6:$E$22,"Ambos")+COUNTIFS('S5'!$B$6:$B$20,$A18,'S5'!$E$6:$E$20,"Víctor")+COUNTIFS('S5'!$B$6:$B$20,$A18,'S5'!$E$6:$E$20,"Ambos")+COUNTIFS('S6'!$B$6:$B$17,$A18,'S6'!$E$6:$E$17,"Víctor")+COUNTIFS('S6'!$B$6:$B$17,$A18,'S6'!$E$6:$E$17,"Ambos")+COUNTIFS('S7'!$B$6:$B$19,$A18,'S7'!$E$6:$E$19,"Víctor")+COUNTIFS('S7'!$B$6:$B$19,$A18,'S7'!$E$6:$E$19,"Ambos")+COUNTIFS('S8'!$B$6:$B$23,$A18,'S8'!$E$6:$E$23,"Víctor")+COUNTIFS('S8'!$B$6:$B$23,$A18,'S8'!$E$6:$E$23,"Ambos")+COUNTIFS('S9'!$B$6:$B$15,$A18,'S9'!$E$6:$E$15,"Víctor")+COUNTIFS('S9'!$B$6:$B$15,$A18,'S9'!$E$6:$E$15,"Ambos")+COUNTIFS('S10'!$B$6:$B$13,$A18,'S10'!$E$6:$E$13,"Víctor")+COUNTIFS('S10'!$B$6:$B$13,$A18,'S10'!$E$6:$E$13,"Ambos")+COUNTIFS('Holgura'!$B$6:$B$11,$A18,'Holgura'!$E$6:$E$11,"Víctor")+COUNTIFS('Holgura'!$B$6:$B$11,$A18,'Holgura'!$E$6:$E$11,"Ambos")+COUNTIFS('Entrega'!$B$6:$B$9,$A18,'Entrega'!$E$6:$E$9,"Víctor")+COUNTIFS('Entrega'!$B$6:$B$9,$A18,'Entrega'!$E$6:$E$9,"Ambos")+COUNTIFS('Defensa'!$B$6:$B$10,$A18,'Defensa'!$E$6:$E$10,"Víctor")+COUNTIFS('Defensa'!$B$6:$B$10,$A18,'Defensa'!$E$6:$E$10,"Ambos")</f>
         <v/>
       </c>
       <c r="G18" s="21">
-        <f>COUNTIFS('S1'!$B$6:$B$32,$A18,'S1'!$E$6:$E$32,"Diego")+COUNTIFS('S1'!$B$6:$B$32,$A18,'S1'!$E$6:$E$32,"Ambos")+COUNTIFS('S2'!$B$6:$B$23,$A18,'S2'!$E$6:$E$23,"Diego")+COUNTIFS('S2'!$B$6:$B$23,$A18,'S2'!$E$6:$E$23,"Ambos")+COUNTIFS('S3'!$B$6:$B$19,$A18,'S3'!$E$6:$E$19,"Diego")+COUNTIFS('S3'!$B$6:$B$19,$A18,'S3'!$E$6:$E$19,"Ambos")+COUNTIFS('S4'!$B$6:$B$20,$A18,'S4'!$E$6:$E$20,"Diego")+COUNTIFS('S4'!$B$6:$B$20,$A18,'S4'!$E$6:$E$20,"Ambos")+COUNTIFS('S5'!$B$6:$B$20,$A18,'S5'!$E$6:$E$20,"Diego")+COUNTIFS('S5'!$B$6:$B$20,$A18,'S5'!$E$6:$E$20,"Ambos")+COUNTIFS('S6'!$B$6:$B$17,$A18,'S6'!$E$6:$E$17,"Diego")+COUNTIFS('S6'!$B$6:$B$17,$A18,'S6'!$E$6:$E$17,"Ambos")+COUNTIFS('S7'!$B$6:$B$19,$A18,'S7'!$E$6:$E$19,"Diego")+COUNTIFS('S7'!$B$6:$B$19,$A18,'S7'!$E$6:$E$19,"Ambos")+COUNTIFS('S8'!$B$6:$B$23,$A18,'S8'!$E$6:$E$23,"Diego")+COUNTIFS('S8'!$B$6:$B$23,$A18,'S8'!$E$6:$E$23,"Ambos")+COUNTIFS('S9'!$B$6:$B$15,$A18,'S9'!$E$6:$E$15,"Diego")+COUNTIFS('S9'!$B$6:$B$15,$A18,'S9'!$E$6:$E$15,"Ambos")+COUNTIFS('S10'!$B$6:$B$13,$A18,'S10'!$E$6:$E$13,"Diego")+COUNTIFS('S10'!$B$6:$B$13,$A18,'S10'!$E$6:$E$13,"Ambos")+COUNTIFS('Holgura'!$B$6:$B$11,$A18,'Holgura'!$E$6:$E$11,"Diego")+COUNTIFS('Holgura'!$B$6:$B$11,$A18,'Holgura'!$E$6:$E$11,"Ambos")+COUNTIFS('Entrega'!$B$6:$B$9,$A18,'Entrega'!$E$6:$E$9,"Diego")+COUNTIFS('Entrega'!$B$6:$B$9,$A18,'Entrega'!$E$6:$E$9,"Ambos")+COUNTIFS('Defensa'!$B$6:$B$10,$A18,'Defensa'!$E$6:$E$10,"Diego")+COUNTIFS('Defensa'!$B$6:$B$10,$A18,'Defensa'!$E$6:$E$10,"Ambos")</f>
+        <f>COUNTIFS('S1'!$B$6:$B$32,$A18,'S1'!$E$6:$E$32,"Diego")+COUNTIFS('S1'!$B$6:$B$32,$A18,'S1'!$E$6:$E$32,"Ambos")+COUNTIFS('S2'!$B$6:$B$23,$A18,'S2'!$E$6:$E$23,"Diego")+COUNTIFS('S2'!$B$6:$B$23,$A18,'S2'!$E$6:$E$23,"Ambos")+COUNTIFS('S3'!$B$6:$B$24,$A18,'S3'!$E$6:$E$24,"Diego")+COUNTIFS('S3'!$B$6:$B$24,$A18,'S3'!$E$6:$E$24,"Ambos")+COUNTIFS('S4'!$B$6:$B$22,$A18,'S4'!$E$6:$E$22,"Diego")+COUNTIFS('S4'!$B$6:$B$22,$A18,'S4'!$E$6:$E$22,"Ambos")+COUNTIFS('S5'!$B$6:$B$20,$A18,'S5'!$E$6:$E$20,"Diego")+COUNTIFS('S5'!$B$6:$B$20,$A18,'S5'!$E$6:$E$20,"Ambos")+COUNTIFS('S6'!$B$6:$B$17,$A18,'S6'!$E$6:$E$17,"Diego")+COUNTIFS('S6'!$B$6:$B$17,$A18,'S6'!$E$6:$E$17,"Ambos")+COUNTIFS('S7'!$B$6:$B$19,$A18,'S7'!$E$6:$E$19,"Diego")+COUNTIFS('S7'!$B$6:$B$19,$A18,'S7'!$E$6:$E$19,"Ambos")+COUNTIFS('S8'!$B$6:$B$23,$A18,'S8'!$E$6:$E$23,"Diego")+COUNTIFS('S8'!$B$6:$B$23,$A18,'S8'!$E$6:$E$23,"Ambos")+COUNTIFS('S9'!$B$6:$B$15,$A18,'S9'!$E$6:$E$15,"Diego")+COUNTIFS('S9'!$B$6:$B$15,$A18,'S9'!$E$6:$E$15,"Ambos")+COUNTIFS('S10'!$B$6:$B$13,$A18,'S10'!$E$6:$E$13,"Diego")+COUNTIFS('S10'!$B$6:$B$13,$A18,'S10'!$E$6:$E$13,"Ambos")+COUNTIFS('Holgura'!$B$6:$B$11,$A18,'Holgura'!$E$6:$E$11,"Diego")+COUNTIFS('Holgura'!$B$6:$B$11,$A18,'Holgura'!$E$6:$E$11,"Ambos")+COUNTIFS('Entrega'!$B$6:$B$9,$A18,'Entrega'!$E$6:$E$9,"Diego")+COUNTIFS('Entrega'!$B$6:$B$9,$A18,'Entrega'!$E$6:$E$9,"Ambos")+COUNTIFS('Defensa'!$B$6:$B$10,$A18,'Defensa'!$E$6:$E$10,"Diego")+COUNTIFS('Defensa'!$B$6:$B$10,$A18,'Defensa'!$E$6:$E$10,"Ambos")</f>
         <v/>
       </c>
     </row>
@@ -9086,19 +9107,19 @@
         <v/>
       </c>
       <c r="D19" s="21">
-        <f>SUMIFS('S1'!$I$6:$I$32,'S1'!$B$6:$B$32,$A19,'S1'!$E$6:$E$32,"Víctor")+SUMIFS('S1'!$I$6:$I$32,'S1'!$B$6:$B$32,$A19,'S1'!$E$6:$E$32,"Ambos")+SUMIFS('S2'!$I$6:$I$23,'S2'!$B$6:$B$23,$A19,'S2'!$E$6:$E$23,"Víctor")+SUMIFS('S2'!$I$6:$I$23,'S2'!$B$6:$B$23,$A19,'S2'!$E$6:$E$23,"Ambos")+SUMIFS('S3'!$I$6:$I$19,'S3'!$B$6:$B$19,$A19,'S3'!$E$6:$E$19,"Víctor")+SUMIFS('S3'!$I$6:$I$19,'S3'!$B$6:$B$19,$A19,'S3'!$E$6:$E$19,"Ambos")+SUMIFS('S4'!$I$6:$I$20,'S4'!$B$6:$B$20,$A19,'S4'!$E$6:$E$20,"Víctor")+SUMIFS('S4'!$I$6:$I$20,'S4'!$B$6:$B$20,$A19,'S4'!$E$6:$E$20,"Ambos")+SUMIFS('S5'!$I$6:$I$20,'S5'!$B$6:$B$20,$A19,'S5'!$E$6:$E$20,"Víctor")+SUMIFS('S5'!$I$6:$I$20,'S5'!$B$6:$B$20,$A19,'S5'!$E$6:$E$20,"Ambos")+SUMIFS('S6'!$I$6:$I$17,'S6'!$B$6:$B$17,$A19,'S6'!$E$6:$E$17,"Víctor")+SUMIFS('S6'!$I$6:$I$17,'S6'!$B$6:$B$17,$A19,'S6'!$E$6:$E$17,"Ambos")+SUMIFS('S7'!$I$6:$I$19,'S7'!$B$6:$B$19,$A19,'S7'!$E$6:$E$19,"Víctor")+SUMIFS('S7'!$I$6:$I$19,'S7'!$B$6:$B$19,$A19,'S7'!$E$6:$E$19,"Ambos")+SUMIFS('S8'!$I$6:$I$23,'S8'!$B$6:$B$23,$A19,'S8'!$E$6:$E$23,"Víctor")+SUMIFS('S8'!$I$6:$I$23,'S8'!$B$6:$B$23,$A19,'S8'!$E$6:$E$23,"Ambos")+SUMIFS('S9'!$I$6:$I$15,'S9'!$B$6:$B$15,$A19,'S9'!$E$6:$E$15,"Víctor")+SUMIFS('S9'!$I$6:$I$15,'S9'!$B$6:$B$15,$A19,'S9'!$E$6:$E$15,"Ambos")+SUMIFS('S10'!$I$6:$I$13,'S10'!$B$6:$B$13,$A19,'S10'!$E$6:$E$13,"Víctor")+SUMIFS('S10'!$I$6:$I$13,'S10'!$B$6:$B$13,$A19,'S10'!$E$6:$E$13,"Ambos")+SUMIFS('Holgura'!$I$6:$I$11,'Holgura'!$B$6:$B$11,$A19,'Holgura'!$E$6:$E$11,"Víctor")+SUMIFS('Holgura'!$I$6:$I$11,'Holgura'!$B$6:$B$11,$A19,'Holgura'!$E$6:$E$11,"Ambos")+SUMIFS('Entrega'!$I$6:$I$9,'Entrega'!$B$6:$B$9,$A19,'Entrega'!$E$6:$E$9,"Víctor")+SUMIFS('Entrega'!$I$6:$I$9,'Entrega'!$B$6:$B$9,$A19,'Entrega'!$E$6:$E$9,"Ambos")+SUMIFS('Defensa'!$I$6:$I$10,'Defensa'!$B$6:$B$10,$A19,'Defensa'!$E$6:$E$10,"Víctor")+SUMIFS('Defensa'!$I$6:$I$10,'Defensa'!$B$6:$B$10,$A19,'Defensa'!$E$6:$E$10,"Ambos")</f>
+        <f>SUMIFS('S1'!$I$6:$I$32,'S1'!$B$6:$B$32,$A19,'S1'!$E$6:$E$32,"Víctor")+SUMIFS('S1'!$I$6:$I$32,'S1'!$B$6:$B$32,$A19,'S1'!$E$6:$E$32,"Ambos")+SUMIFS('S2'!$I$6:$I$23,'S2'!$B$6:$B$23,$A19,'S2'!$E$6:$E$23,"Víctor")+SUMIFS('S2'!$I$6:$I$23,'S2'!$B$6:$B$23,$A19,'S2'!$E$6:$E$23,"Ambos")+SUMIFS('S3'!$I$6:$I$24,'S3'!$B$6:$B$24,$A19,'S3'!$E$6:$E$24,"Víctor")+SUMIFS('S3'!$I$6:$I$24,'S3'!$B$6:$B$24,$A19,'S3'!$E$6:$E$24,"Ambos")+SUMIFS('S4'!$I$6:$I$22,'S4'!$B$6:$B$22,$A19,'S4'!$E$6:$E$22,"Víctor")+SUMIFS('S4'!$I$6:$I$22,'S4'!$B$6:$B$22,$A19,'S4'!$E$6:$E$22,"Ambos")+SUMIFS('S5'!$I$6:$I$20,'S5'!$B$6:$B$20,$A19,'S5'!$E$6:$E$20,"Víctor")+SUMIFS('S5'!$I$6:$I$20,'S5'!$B$6:$B$20,$A19,'S5'!$E$6:$E$20,"Ambos")+SUMIFS('S6'!$I$6:$I$17,'S6'!$B$6:$B$17,$A19,'S6'!$E$6:$E$17,"Víctor")+SUMIFS('S6'!$I$6:$I$17,'S6'!$B$6:$B$17,$A19,'S6'!$E$6:$E$17,"Ambos")+SUMIFS('S7'!$I$6:$I$19,'S7'!$B$6:$B$19,$A19,'S7'!$E$6:$E$19,"Víctor")+SUMIFS('S7'!$I$6:$I$19,'S7'!$B$6:$B$19,$A19,'S7'!$E$6:$E$19,"Ambos")+SUMIFS('S8'!$I$6:$I$23,'S8'!$B$6:$B$23,$A19,'S8'!$E$6:$E$23,"Víctor")+SUMIFS('S8'!$I$6:$I$23,'S8'!$B$6:$B$23,$A19,'S8'!$E$6:$E$23,"Ambos")+SUMIFS('S9'!$I$6:$I$15,'S9'!$B$6:$B$15,$A19,'S9'!$E$6:$E$15,"Víctor")+SUMIFS('S9'!$I$6:$I$15,'S9'!$B$6:$B$15,$A19,'S9'!$E$6:$E$15,"Ambos")+SUMIFS('S10'!$I$6:$I$13,'S10'!$B$6:$B$13,$A19,'S10'!$E$6:$E$13,"Víctor")+SUMIFS('S10'!$I$6:$I$13,'S10'!$B$6:$B$13,$A19,'S10'!$E$6:$E$13,"Ambos")+SUMIFS('Holgura'!$I$6:$I$11,'Holgura'!$B$6:$B$11,$A19,'Holgura'!$E$6:$E$11,"Víctor")+SUMIFS('Holgura'!$I$6:$I$11,'Holgura'!$B$6:$B$11,$A19,'Holgura'!$E$6:$E$11,"Ambos")+SUMIFS('Entrega'!$I$6:$I$9,'Entrega'!$B$6:$B$9,$A19,'Entrega'!$E$6:$E$9,"Víctor")+SUMIFS('Entrega'!$I$6:$I$9,'Entrega'!$B$6:$B$9,$A19,'Entrega'!$E$6:$E$9,"Ambos")+SUMIFS('Defensa'!$I$6:$I$10,'Defensa'!$B$6:$B$10,$A19,'Defensa'!$E$6:$E$10,"Víctor")+SUMIFS('Defensa'!$I$6:$I$10,'Defensa'!$B$6:$B$10,$A19,'Defensa'!$E$6:$E$10,"Ambos")</f>
         <v/>
       </c>
       <c r="E19" s="21">
-        <f>SUMIFS('S1'!$I$6:$I$32,'S1'!$B$6:$B$32,$A19,'S1'!$E$6:$E$32,"Diego")+SUMIFS('S1'!$I$6:$I$32,'S1'!$B$6:$B$32,$A19,'S1'!$E$6:$E$32,"Ambos")+SUMIFS('S2'!$I$6:$I$23,'S2'!$B$6:$B$23,$A19,'S2'!$E$6:$E$23,"Diego")+SUMIFS('S2'!$I$6:$I$23,'S2'!$B$6:$B$23,$A19,'S2'!$E$6:$E$23,"Ambos")+SUMIFS('S3'!$I$6:$I$19,'S3'!$B$6:$B$19,$A19,'S3'!$E$6:$E$19,"Diego")+SUMIFS('S3'!$I$6:$I$19,'S3'!$B$6:$B$19,$A19,'S3'!$E$6:$E$19,"Ambos")+SUMIFS('S4'!$I$6:$I$20,'S4'!$B$6:$B$20,$A19,'S4'!$E$6:$E$20,"Diego")+SUMIFS('S4'!$I$6:$I$20,'S4'!$B$6:$B$20,$A19,'S4'!$E$6:$E$20,"Ambos")+SUMIFS('S5'!$I$6:$I$20,'S5'!$B$6:$B$20,$A19,'S5'!$E$6:$E$20,"Diego")+SUMIFS('S5'!$I$6:$I$20,'S5'!$B$6:$B$20,$A19,'S5'!$E$6:$E$20,"Ambos")+SUMIFS('S6'!$I$6:$I$17,'S6'!$B$6:$B$17,$A19,'S6'!$E$6:$E$17,"Diego")+SUMIFS('S6'!$I$6:$I$17,'S6'!$B$6:$B$17,$A19,'S6'!$E$6:$E$17,"Ambos")+SUMIFS('S7'!$I$6:$I$19,'S7'!$B$6:$B$19,$A19,'S7'!$E$6:$E$19,"Diego")+SUMIFS('S7'!$I$6:$I$19,'S7'!$B$6:$B$19,$A19,'S7'!$E$6:$E$19,"Ambos")+SUMIFS('S8'!$I$6:$I$23,'S8'!$B$6:$B$23,$A19,'S8'!$E$6:$E$23,"Diego")+SUMIFS('S8'!$I$6:$I$23,'S8'!$B$6:$B$23,$A19,'S8'!$E$6:$E$23,"Ambos")+SUMIFS('S9'!$I$6:$I$15,'S9'!$B$6:$B$15,$A19,'S9'!$E$6:$E$15,"Diego")+SUMIFS('S9'!$I$6:$I$15,'S9'!$B$6:$B$15,$A19,'S9'!$E$6:$E$15,"Ambos")+SUMIFS('S10'!$I$6:$I$13,'S10'!$B$6:$B$13,$A19,'S10'!$E$6:$E$13,"Diego")+SUMIFS('S10'!$I$6:$I$13,'S10'!$B$6:$B$13,$A19,'S10'!$E$6:$E$13,"Ambos")+SUMIFS('Holgura'!$I$6:$I$11,'Holgura'!$B$6:$B$11,$A19,'Holgura'!$E$6:$E$11,"Diego")+SUMIFS('Holgura'!$I$6:$I$11,'Holgura'!$B$6:$B$11,$A19,'Holgura'!$E$6:$E$11,"Ambos")+SUMIFS('Entrega'!$I$6:$I$9,'Entrega'!$B$6:$B$9,$A19,'Entrega'!$E$6:$E$9,"Diego")+SUMIFS('Entrega'!$I$6:$I$9,'Entrega'!$B$6:$B$9,$A19,'Entrega'!$E$6:$E$9,"Ambos")+SUMIFS('Defensa'!$I$6:$I$10,'Defensa'!$B$6:$B$10,$A19,'Defensa'!$E$6:$E$10,"Diego")+SUMIFS('Defensa'!$I$6:$I$10,'Defensa'!$B$6:$B$10,$A19,'Defensa'!$E$6:$E$10,"Ambos")</f>
+        <f>SUMIFS('S1'!$I$6:$I$32,'S1'!$B$6:$B$32,$A19,'S1'!$E$6:$E$32,"Diego")+SUMIFS('S1'!$I$6:$I$32,'S1'!$B$6:$B$32,$A19,'S1'!$E$6:$E$32,"Ambos")+SUMIFS('S2'!$I$6:$I$23,'S2'!$B$6:$B$23,$A19,'S2'!$E$6:$E$23,"Diego")+SUMIFS('S2'!$I$6:$I$23,'S2'!$B$6:$B$23,$A19,'S2'!$E$6:$E$23,"Ambos")+SUMIFS('S3'!$I$6:$I$24,'S3'!$B$6:$B$24,$A19,'S3'!$E$6:$E$24,"Diego")+SUMIFS('S3'!$I$6:$I$24,'S3'!$B$6:$B$24,$A19,'S3'!$E$6:$E$24,"Ambos")+SUMIFS('S4'!$I$6:$I$22,'S4'!$B$6:$B$22,$A19,'S4'!$E$6:$E$22,"Diego")+SUMIFS('S4'!$I$6:$I$22,'S4'!$B$6:$B$22,$A19,'S4'!$E$6:$E$22,"Ambos")+SUMIFS('S5'!$I$6:$I$20,'S5'!$B$6:$B$20,$A19,'S5'!$E$6:$E$20,"Diego")+SUMIFS('S5'!$I$6:$I$20,'S5'!$B$6:$B$20,$A19,'S5'!$E$6:$E$20,"Ambos")+SUMIFS('S6'!$I$6:$I$17,'S6'!$B$6:$B$17,$A19,'S6'!$E$6:$E$17,"Diego")+SUMIFS('S6'!$I$6:$I$17,'S6'!$B$6:$B$17,$A19,'S6'!$E$6:$E$17,"Ambos")+SUMIFS('S7'!$I$6:$I$19,'S7'!$B$6:$B$19,$A19,'S7'!$E$6:$E$19,"Diego")+SUMIFS('S7'!$I$6:$I$19,'S7'!$B$6:$B$19,$A19,'S7'!$E$6:$E$19,"Ambos")+SUMIFS('S8'!$I$6:$I$23,'S8'!$B$6:$B$23,$A19,'S8'!$E$6:$E$23,"Diego")+SUMIFS('S8'!$I$6:$I$23,'S8'!$B$6:$B$23,$A19,'S8'!$E$6:$E$23,"Ambos")+SUMIFS('S9'!$I$6:$I$15,'S9'!$B$6:$B$15,$A19,'S9'!$E$6:$E$15,"Diego")+SUMIFS('S9'!$I$6:$I$15,'S9'!$B$6:$B$15,$A19,'S9'!$E$6:$E$15,"Ambos")+SUMIFS('S10'!$I$6:$I$13,'S10'!$B$6:$B$13,$A19,'S10'!$E$6:$E$13,"Diego")+SUMIFS('S10'!$I$6:$I$13,'S10'!$B$6:$B$13,$A19,'S10'!$E$6:$E$13,"Ambos")+SUMIFS('Holgura'!$I$6:$I$11,'Holgura'!$B$6:$B$11,$A19,'Holgura'!$E$6:$E$11,"Diego")+SUMIFS('Holgura'!$I$6:$I$11,'Holgura'!$B$6:$B$11,$A19,'Holgura'!$E$6:$E$11,"Ambos")+SUMIFS('Entrega'!$I$6:$I$9,'Entrega'!$B$6:$B$9,$A19,'Entrega'!$E$6:$E$9,"Diego")+SUMIFS('Entrega'!$I$6:$I$9,'Entrega'!$B$6:$B$9,$A19,'Entrega'!$E$6:$E$9,"Ambos")+SUMIFS('Defensa'!$I$6:$I$10,'Defensa'!$B$6:$B$10,$A19,'Defensa'!$E$6:$E$10,"Diego")+SUMIFS('Defensa'!$I$6:$I$10,'Defensa'!$B$6:$B$10,$A19,'Defensa'!$E$6:$E$10,"Ambos")</f>
         <v/>
       </c>
       <c r="F19" s="21">
-        <f>COUNTIFS('S1'!$B$6:$B$32,$A19,'S1'!$E$6:$E$32,"Víctor")+COUNTIFS('S1'!$B$6:$B$32,$A19,'S1'!$E$6:$E$32,"Ambos")+COUNTIFS('S2'!$B$6:$B$23,$A19,'S2'!$E$6:$E$23,"Víctor")+COUNTIFS('S2'!$B$6:$B$23,$A19,'S2'!$E$6:$E$23,"Ambos")+COUNTIFS('S3'!$B$6:$B$19,$A19,'S3'!$E$6:$E$19,"Víctor")+COUNTIFS('S3'!$B$6:$B$19,$A19,'S3'!$E$6:$E$19,"Ambos")+COUNTIFS('S4'!$B$6:$B$20,$A19,'S4'!$E$6:$E$20,"Víctor")+COUNTIFS('S4'!$B$6:$B$20,$A19,'S4'!$E$6:$E$20,"Ambos")+COUNTIFS('S5'!$B$6:$B$20,$A19,'S5'!$E$6:$E$20,"Víctor")+COUNTIFS('S5'!$B$6:$B$20,$A19,'S5'!$E$6:$E$20,"Ambos")+COUNTIFS('S6'!$B$6:$B$17,$A19,'S6'!$E$6:$E$17,"Víctor")+COUNTIFS('S6'!$B$6:$B$17,$A19,'S6'!$E$6:$E$17,"Ambos")+COUNTIFS('S7'!$B$6:$B$19,$A19,'S7'!$E$6:$E$19,"Víctor")+COUNTIFS('S7'!$B$6:$B$19,$A19,'S7'!$E$6:$E$19,"Ambos")+COUNTIFS('S8'!$B$6:$B$23,$A19,'S8'!$E$6:$E$23,"Víctor")+COUNTIFS('S8'!$B$6:$B$23,$A19,'S8'!$E$6:$E$23,"Ambos")+COUNTIFS('S9'!$B$6:$B$15,$A19,'S9'!$E$6:$E$15,"Víctor")+COUNTIFS('S9'!$B$6:$B$15,$A19,'S9'!$E$6:$E$15,"Ambos")+COUNTIFS('S10'!$B$6:$B$13,$A19,'S10'!$E$6:$E$13,"Víctor")+COUNTIFS('S10'!$B$6:$B$13,$A19,'S10'!$E$6:$E$13,"Ambos")+COUNTIFS('Holgura'!$B$6:$B$11,$A19,'Holgura'!$E$6:$E$11,"Víctor")+COUNTIFS('Holgura'!$B$6:$B$11,$A19,'Holgura'!$E$6:$E$11,"Ambos")+COUNTIFS('Entrega'!$B$6:$B$9,$A19,'Entrega'!$E$6:$E$9,"Víctor")+COUNTIFS('Entrega'!$B$6:$B$9,$A19,'Entrega'!$E$6:$E$9,"Ambos")+COUNTIFS('Defensa'!$B$6:$B$10,$A19,'Defensa'!$E$6:$E$10,"Víctor")+COUNTIFS('Defensa'!$B$6:$B$10,$A19,'Defensa'!$E$6:$E$10,"Ambos")</f>
+        <f>COUNTIFS('S1'!$B$6:$B$32,$A19,'S1'!$E$6:$E$32,"Víctor")+COUNTIFS('S1'!$B$6:$B$32,$A19,'S1'!$E$6:$E$32,"Ambos")+COUNTIFS('S2'!$B$6:$B$23,$A19,'S2'!$E$6:$E$23,"Víctor")+COUNTIFS('S2'!$B$6:$B$23,$A19,'S2'!$E$6:$E$23,"Ambos")+COUNTIFS('S3'!$B$6:$B$24,$A19,'S3'!$E$6:$E$24,"Víctor")+COUNTIFS('S3'!$B$6:$B$24,$A19,'S3'!$E$6:$E$24,"Ambos")+COUNTIFS('S4'!$B$6:$B$22,$A19,'S4'!$E$6:$E$22,"Víctor")+COUNTIFS('S4'!$B$6:$B$22,$A19,'S4'!$E$6:$E$22,"Ambos")+COUNTIFS('S5'!$B$6:$B$20,$A19,'S5'!$E$6:$E$20,"Víctor")+COUNTIFS('S5'!$B$6:$B$20,$A19,'S5'!$E$6:$E$20,"Ambos")+COUNTIFS('S6'!$B$6:$B$17,$A19,'S6'!$E$6:$E$17,"Víctor")+COUNTIFS('S6'!$B$6:$B$17,$A19,'S6'!$E$6:$E$17,"Ambos")+COUNTIFS('S7'!$B$6:$B$19,$A19,'S7'!$E$6:$E$19,"Víctor")+COUNTIFS('S7'!$B$6:$B$19,$A19,'S7'!$E$6:$E$19,"Ambos")+COUNTIFS('S8'!$B$6:$B$23,$A19,'S8'!$E$6:$E$23,"Víctor")+COUNTIFS('S8'!$B$6:$B$23,$A19,'S8'!$E$6:$E$23,"Ambos")+COUNTIFS('S9'!$B$6:$B$15,$A19,'S9'!$E$6:$E$15,"Víctor")+COUNTIFS('S9'!$B$6:$B$15,$A19,'S9'!$E$6:$E$15,"Ambos")+COUNTIFS('S10'!$B$6:$B$13,$A19,'S10'!$E$6:$E$13,"Víctor")+COUNTIFS('S10'!$B$6:$B$13,$A19,'S10'!$E$6:$E$13,"Ambos")+COUNTIFS('Holgura'!$B$6:$B$11,$A19,'Holgura'!$E$6:$E$11,"Víctor")+COUNTIFS('Holgura'!$B$6:$B$11,$A19,'Holgura'!$E$6:$E$11,"Ambos")+COUNTIFS('Entrega'!$B$6:$B$9,$A19,'Entrega'!$E$6:$E$9,"Víctor")+COUNTIFS('Entrega'!$B$6:$B$9,$A19,'Entrega'!$E$6:$E$9,"Ambos")+COUNTIFS('Defensa'!$B$6:$B$10,$A19,'Defensa'!$E$6:$E$10,"Víctor")+COUNTIFS('Defensa'!$B$6:$B$10,$A19,'Defensa'!$E$6:$E$10,"Ambos")</f>
         <v/>
       </c>
       <c r="G19" s="21">
-        <f>COUNTIFS('S1'!$B$6:$B$32,$A19,'S1'!$E$6:$E$32,"Diego")+COUNTIFS('S1'!$B$6:$B$32,$A19,'S1'!$E$6:$E$32,"Ambos")+COUNTIFS('S2'!$B$6:$B$23,$A19,'S2'!$E$6:$E$23,"Diego")+COUNTIFS('S2'!$B$6:$B$23,$A19,'S2'!$E$6:$E$23,"Ambos")+COUNTIFS('S3'!$B$6:$B$19,$A19,'S3'!$E$6:$E$19,"Diego")+COUNTIFS('S3'!$B$6:$B$19,$A19,'S3'!$E$6:$E$19,"Ambos")+COUNTIFS('S4'!$B$6:$B$20,$A19,'S4'!$E$6:$E$20,"Diego")+COUNTIFS('S4'!$B$6:$B$20,$A19,'S4'!$E$6:$E$20,"Ambos")+COUNTIFS('S5'!$B$6:$B$20,$A19,'S5'!$E$6:$E$20,"Diego")+COUNTIFS('S5'!$B$6:$B$20,$A19,'S5'!$E$6:$E$20,"Ambos")+COUNTIFS('S6'!$B$6:$B$17,$A19,'S6'!$E$6:$E$17,"Diego")+COUNTIFS('S6'!$B$6:$B$17,$A19,'S6'!$E$6:$E$17,"Ambos")+COUNTIFS('S7'!$B$6:$B$19,$A19,'S7'!$E$6:$E$19,"Diego")+COUNTIFS('S7'!$B$6:$B$19,$A19,'S7'!$E$6:$E$19,"Ambos")+COUNTIFS('S8'!$B$6:$B$23,$A19,'S8'!$E$6:$E$23,"Diego")+COUNTIFS('S8'!$B$6:$B$23,$A19,'S8'!$E$6:$E$23,"Ambos")+COUNTIFS('S9'!$B$6:$B$15,$A19,'S9'!$E$6:$E$15,"Diego")+COUNTIFS('S9'!$B$6:$B$15,$A19,'S9'!$E$6:$E$15,"Ambos")+COUNTIFS('S10'!$B$6:$B$13,$A19,'S10'!$E$6:$E$13,"Diego")+COUNTIFS('S10'!$B$6:$B$13,$A19,'S10'!$E$6:$E$13,"Ambos")+COUNTIFS('Holgura'!$B$6:$B$11,$A19,'Holgura'!$E$6:$E$11,"Diego")+COUNTIFS('Holgura'!$B$6:$B$11,$A19,'Holgura'!$E$6:$E$11,"Ambos")+COUNTIFS('Entrega'!$B$6:$B$9,$A19,'Entrega'!$E$6:$E$9,"Diego")+COUNTIFS('Entrega'!$B$6:$B$9,$A19,'Entrega'!$E$6:$E$9,"Ambos")+COUNTIFS('Defensa'!$B$6:$B$10,$A19,'Defensa'!$E$6:$E$10,"Diego")+COUNTIFS('Defensa'!$B$6:$B$10,$A19,'Defensa'!$E$6:$E$10,"Ambos")</f>
+        <f>COUNTIFS('S1'!$B$6:$B$32,$A19,'S1'!$E$6:$E$32,"Diego")+COUNTIFS('S1'!$B$6:$B$32,$A19,'S1'!$E$6:$E$32,"Ambos")+COUNTIFS('S2'!$B$6:$B$23,$A19,'S2'!$E$6:$E$23,"Diego")+COUNTIFS('S2'!$B$6:$B$23,$A19,'S2'!$E$6:$E$23,"Ambos")+COUNTIFS('S3'!$B$6:$B$24,$A19,'S3'!$E$6:$E$24,"Diego")+COUNTIFS('S3'!$B$6:$B$24,$A19,'S3'!$E$6:$E$24,"Ambos")+COUNTIFS('S4'!$B$6:$B$22,$A19,'S4'!$E$6:$E$22,"Diego")+COUNTIFS('S4'!$B$6:$B$22,$A19,'S4'!$E$6:$E$22,"Ambos")+COUNTIFS('S5'!$B$6:$B$20,$A19,'S5'!$E$6:$E$20,"Diego")+COUNTIFS('S5'!$B$6:$B$20,$A19,'S5'!$E$6:$E$20,"Ambos")+COUNTIFS('S6'!$B$6:$B$17,$A19,'S6'!$E$6:$E$17,"Diego")+COUNTIFS('S6'!$B$6:$B$17,$A19,'S6'!$E$6:$E$17,"Ambos")+COUNTIFS('S7'!$B$6:$B$19,$A19,'S7'!$E$6:$E$19,"Diego")+COUNTIFS('S7'!$B$6:$B$19,$A19,'S7'!$E$6:$E$19,"Ambos")+COUNTIFS('S8'!$B$6:$B$23,$A19,'S8'!$E$6:$E$23,"Diego")+COUNTIFS('S8'!$B$6:$B$23,$A19,'S8'!$E$6:$E$23,"Ambos")+COUNTIFS('S9'!$B$6:$B$15,$A19,'S9'!$E$6:$E$15,"Diego")+COUNTIFS('S9'!$B$6:$B$15,$A19,'S9'!$E$6:$E$15,"Ambos")+COUNTIFS('S10'!$B$6:$B$13,$A19,'S10'!$E$6:$E$13,"Diego")+COUNTIFS('S10'!$B$6:$B$13,$A19,'S10'!$E$6:$E$13,"Ambos")+COUNTIFS('Holgura'!$B$6:$B$11,$A19,'Holgura'!$E$6:$E$11,"Diego")+COUNTIFS('Holgura'!$B$6:$B$11,$A19,'Holgura'!$E$6:$E$11,"Ambos")+COUNTIFS('Entrega'!$B$6:$B$9,$A19,'Entrega'!$E$6:$E$9,"Diego")+COUNTIFS('Entrega'!$B$6:$B$9,$A19,'Entrega'!$E$6:$E$9,"Ambos")+COUNTIFS('Defensa'!$B$6:$B$10,$A19,'Defensa'!$E$6:$E$10,"Diego")+COUNTIFS('Defensa'!$B$6:$B$10,$A19,'Defensa'!$E$6:$E$10,"Ambos")</f>
         <v/>
       </c>
     </row>
@@ -9115,19 +9136,19 @@
         <v/>
       </c>
       <c r="D20" s="21">
-        <f>SUMIFS('S1'!$I$6:$I$32,'S1'!$B$6:$B$32,$A20,'S1'!$E$6:$E$32,"Víctor")+SUMIFS('S1'!$I$6:$I$32,'S1'!$B$6:$B$32,$A20,'S1'!$E$6:$E$32,"Ambos")+SUMIFS('S2'!$I$6:$I$23,'S2'!$B$6:$B$23,$A20,'S2'!$E$6:$E$23,"Víctor")+SUMIFS('S2'!$I$6:$I$23,'S2'!$B$6:$B$23,$A20,'S2'!$E$6:$E$23,"Ambos")+SUMIFS('S3'!$I$6:$I$19,'S3'!$B$6:$B$19,$A20,'S3'!$E$6:$E$19,"Víctor")+SUMIFS('S3'!$I$6:$I$19,'S3'!$B$6:$B$19,$A20,'S3'!$E$6:$E$19,"Ambos")+SUMIFS('S4'!$I$6:$I$20,'S4'!$B$6:$B$20,$A20,'S4'!$E$6:$E$20,"Víctor")+SUMIFS('S4'!$I$6:$I$20,'S4'!$B$6:$B$20,$A20,'S4'!$E$6:$E$20,"Ambos")+SUMIFS('S5'!$I$6:$I$20,'S5'!$B$6:$B$20,$A20,'S5'!$E$6:$E$20,"Víctor")+SUMIFS('S5'!$I$6:$I$20,'S5'!$B$6:$B$20,$A20,'S5'!$E$6:$E$20,"Ambos")+SUMIFS('S6'!$I$6:$I$17,'S6'!$B$6:$B$17,$A20,'S6'!$E$6:$E$17,"Víctor")+SUMIFS('S6'!$I$6:$I$17,'S6'!$B$6:$B$17,$A20,'S6'!$E$6:$E$17,"Ambos")+SUMIFS('S7'!$I$6:$I$19,'S7'!$B$6:$B$19,$A20,'S7'!$E$6:$E$19,"Víctor")+SUMIFS('S7'!$I$6:$I$19,'S7'!$B$6:$B$19,$A20,'S7'!$E$6:$E$19,"Ambos")+SUMIFS('S8'!$I$6:$I$23,'S8'!$B$6:$B$23,$A20,'S8'!$E$6:$E$23,"Víctor")+SUMIFS('S8'!$I$6:$I$23,'S8'!$B$6:$B$23,$A20,'S8'!$E$6:$E$23,"Ambos")+SUMIFS('S9'!$I$6:$I$15,'S9'!$B$6:$B$15,$A20,'S9'!$E$6:$E$15,"Víctor")+SUMIFS('S9'!$I$6:$I$15,'S9'!$B$6:$B$15,$A20,'S9'!$E$6:$E$15,"Ambos")+SUMIFS('S10'!$I$6:$I$13,'S10'!$B$6:$B$13,$A20,'S10'!$E$6:$E$13,"Víctor")+SUMIFS('S10'!$I$6:$I$13,'S10'!$B$6:$B$13,$A20,'S10'!$E$6:$E$13,"Ambos")+SUMIFS('Holgura'!$I$6:$I$11,'Holgura'!$B$6:$B$11,$A20,'Holgura'!$E$6:$E$11,"Víctor")+SUMIFS('Holgura'!$I$6:$I$11,'Holgura'!$B$6:$B$11,$A20,'Holgura'!$E$6:$E$11,"Ambos")+SUMIFS('Entrega'!$I$6:$I$9,'Entrega'!$B$6:$B$9,$A20,'Entrega'!$E$6:$E$9,"Víctor")+SUMIFS('Entrega'!$I$6:$I$9,'Entrega'!$B$6:$B$9,$A20,'Entrega'!$E$6:$E$9,"Ambos")+SUMIFS('Defensa'!$I$6:$I$10,'Defensa'!$B$6:$B$10,$A20,'Defensa'!$E$6:$E$10,"Víctor")+SUMIFS('Defensa'!$I$6:$I$10,'Defensa'!$B$6:$B$10,$A20,'Defensa'!$E$6:$E$10,"Ambos")</f>
+        <f>SUMIFS('S1'!$I$6:$I$32,'S1'!$B$6:$B$32,$A20,'S1'!$E$6:$E$32,"Víctor")+SUMIFS('S1'!$I$6:$I$32,'S1'!$B$6:$B$32,$A20,'S1'!$E$6:$E$32,"Ambos")+SUMIFS('S2'!$I$6:$I$23,'S2'!$B$6:$B$23,$A20,'S2'!$E$6:$E$23,"Víctor")+SUMIFS('S2'!$I$6:$I$23,'S2'!$B$6:$B$23,$A20,'S2'!$E$6:$E$23,"Ambos")+SUMIFS('S3'!$I$6:$I$24,'S3'!$B$6:$B$24,$A20,'S3'!$E$6:$E$24,"Víctor")+SUMIFS('S3'!$I$6:$I$24,'S3'!$B$6:$B$24,$A20,'S3'!$E$6:$E$24,"Ambos")+SUMIFS('S4'!$I$6:$I$22,'S4'!$B$6:$B$22,$A20,'S4'!$E$6:$E$22,"Víctor")+SUMIFS('S4'!$I$6:$I$22,'S4'!$B$6:$B$22,$A20,'S4'!$E$6:$E$22,"Ambos")+SUMIFS('S5'!$I$6:$I$20,'S5'!$B$6:$B$20,$A20,'S5'!$E$6:$E$20,"Víctor")+SUMIFS('S5'!$I$6:$I$20,'S5'!$B$6:$B$20,$A20,'S5'!$E$6:$E$20,"Ambos")+SUMIFS('S6'!$I$6:$I$17,'S6'!$B$6:$B$17,$A20,'S6'!$E$6:$E$17,"Víctor")+SUMIFS('S6'!$I$6:$I$17,'S6'!$B$6:$B$17,$A20,'S6'!$E$6:$E$17,"Ambos")+SUMIFS('S7'!$I$6:$I$19,'S7'!$B$6:$B$19,$A20,'S7'!$E$6:$E$19,"Víctor")+SUMIFS('S7'!$I$6:$I$19,'S7'!$B$6:$B$19,$A20,'S7'!$E$6:$E$19,"Ambos")+SUMIFS('S8'!$I$6:$I$23,'S8'!$B$6:$B$23,$A20,'S8'!$E$6:$E$23,"Víctor")+SUMIFS('S8'!$I$6:$I$23,'S8'!$B$6:$B$23,$A20,'S8'!$E$6:$E$23,"Ambos")+SUMIFS('S9'!$I$6:$I$15,'S9'!$B$6:$B$15,$A20,'S9'!$E$6:$E$15,"Víctor")+SUMIFS('S9'!$I$6:$I$15,'S9'!$B$6:$B$15,$A20,'S9'!$E$6:$E$15,"Ambos")+SUMIFS('S10'!$I$6:$I$13,'S10'!$B$6:$B$13,$A20,'S10'!$E$6:$E$13,"Víctor")+SUMIFS('S10'!$I$6:$I$13,'S10'!$B$6:$B$13,$A20,'S10'!$E$6:$E$13,"Ambos")+SUMIFS('Holgura'!$I$6:$I$11,'Holgura'!$B$6:$B$11,$A20,'Holgura'!$E$6:$E$11,"Víctor")+SUMIFS('Holgura'!$I$6:$I$11,'Holgura'!$B$6:$B$11,$A20,'Holgura'!$E$6:$E$11,"Ambos")+SUMIFS('Entrega'!$I$6:$I$9,'Entrega'!$B$6:$B$9,$A20,'Entrega'!$E$6:$E$9,"Víctor")+SUMIFS('Entrega'!$I$6:$I$9,'Entrega'!$B$6:$B$9,$A20,'Entrega'!$E$6:$E$9,"Ambos")+SUMIFS('Defensa'!$I$6:$I$10,'Defensa'!$B$6:$B$10,$A20,'Defensa'!$E$6:$E$10,"Víctor")+SUMIFS('Defensa'!$I$6:$I$10,'Defensa'!$B$6:$B$10,$A20,'Defensa'!$E$6:$E$10,"Ambos")</f>
         <v/>
       </c>
       <c r="E20" s="21">
-        <f>SUMIFS('S1'!$I$6:$I$32,'S1'!$B$6:$B$32,$A20,'S1'!$E$6:$E$32,"Diego")+SUMIFS('S1'!$I$6:$I$32,'S1'!$B$6:$B$32,$A20,'S1'!$E$6:$E$32,"Ambos")+SUMIFS('S2'!$I$6:$I$23,'S2'!$B$6:$B$23,$A20,'S2'!$E$6:$E$23,"Diego")+SUMIFS('S2'!$I$6:$I$23,'S2'!$B$6:$B$23,$A20,'S2'!$E$6:$E$23,"Ambos")+SUMIFS('S3'!$I$6:$I$19,'S3'!$B$6:$B$19,$A20,'S3'!$E$6:$E$19,"Diego")+SUMIFS('S3'!$I$6:$I$19,'S3'!$B$6:$B$19,$A20,'S3'!$E$6:$E$19,"Ambos")+SUMIFS('S4'!$I$6:$I$20,'S4'!$B$6:$B$20,$A20,'S4'!$E$6:$E$20,"Diego")+SUMIFS('S4'!$I$6:$I$20,'S4'!$B$6:$B$20,$A20,'S4'!$E$6:$E$20,"Ambos")+SUMIFS('S5'!$I$6:$I$20,'S5'!$B$6:$B$20,$A20,'S5'!$E$6:$E$20,"Diego")+SUMIFS('S5'!$I$6:$I$20,'S5'!$B$6:$B$20,$A20,'S5'!$E$6:$E$20,"Ambos")+SUMIFS('S6'!$I$6:$I$17,'S6'!$B$6:$B$17,$A20,'S6'!$E$6:$E$17,"Diego")+SUMIFS('S6'!$I$6:$I$17,'S6'!$B$6:$B$17,$A20,'S6'!$E$6:$E$17,"Ambos")+SUMIFS('S7'!$I$6:$I$19,'S7'!$B$6:$B$19,$A20,'S7'!$E$6:$E$19,"Diego")+SUMIFS('S7'!$I$6:$I$19,'S7'!$B$6:$B$19,$A20,'S7'!$E$6:$E$19,"Ambos")+SUMIFS('S8'!$I$6:$I$23,'S8'!$B$6:$B$23,$A20,'S8'!$E$6:$E$23,"Diego")+SUMIFS('S8'!$I$6:$I$23,'S8'!$B$6:$B$23,$A20,'S8'!$E$6:$E$23,"Ambos")+SUMIFS('S9'!$I$6:$I$15,'S9'!$B$6:$B$15,$A20,'S9'!$E$6:$E$15,"Diego")+SUMIFS('S9'!$I$6:$I$15,'S9'!$B$6:$B$15,$A20,'S9'!$E$6:$E$15,"Ambos")+SUMIFS('S10'!$I$6:$I$13,'S10'!$B$6:$B$13,$A20,'S10'!$E$6:$E$13,"Diego")+SUMIFS('S10'!$I$6:$I$13,'S10'!$B$6:$B$13,$A20,'S10'!$E$6:$E$13,"Ambos")+SUMIFS('Holgura'!$I$6:$I$11,'Holgura'!$B$6:$B$11,$A20,'Holgura'!$E$6:$E$11,"Diego")+SUMIFS('Holgura'!$I$6:$I$11,'Holgura'!$B$6:$B$11,$A20,'Holgura'!$E$6:$E$11,"Ambos")+SUMIFS('Entrega'!$I$6:$I$9,'Entrega'!$B$6:$B$9,$A20,'Entrega'!$E$6:$E$9,"Diego")+SUMIFS('Entrega'!$I$6:$I$9,'Entrega'!$B$6:$B$9,$A20,'Entrega'!$E$6:$E$9,"Ambos")+SUMIFS('Defensa'!$I$6:$I$10,'Defensa'!$B$6:$B$10,$A20,'Defensa'!$E$6:$E$10,"Diego")+SUMIFS('Defensa'!$I$6:$I$10,'Defensa'!$B$6:$B$10,$A20,'Defensa'!$E$6:$E$10,"Ambos")</f>
+        <f>SUMIFS('S1'!$I$6:$I$32,'S1'!$B$6:$B$32,$A20,'S1'!$E$6:$E$32,"Diego")+SUMIFS('S1'!$I$6:$I$32,'S1'!$B$6:$B$32,$A20,'S1'!$E$6:$E$32,"Ambos")+SUMIFS('S2'!$I$6:$I$23,'S2'!$B$6:$B$23,$A20,'S2'!$E$6:$E$23,"Diego")+SUMIFS('S2'!$I$6:$I$23,'S2'!$B$6:$B$23,$A20,'S2'!$E$6:$E$23,"Ambos")+SUMIFS('S3'!$I$6:$I$24,'S3'!$B$6:$B$24,$A20,'S3'!$E$6:$E$24,"Diego")+SUMIFS('S3'!$I$6:$I$24,'S3'!$B$6:$B$24,$A20,'S3'!$E$6:$E$24,"Ambos")+SUMIFS('S4'!$I$6:$I$22,'S4'!$B$6:$B$22,$A20,'S4'!$E$6:$E$22,"Diego")+SUMIFS('S4'!$I$6:$I$22,'S4'!$B$6:$B$22,$A20,'S4'!$E$6:$E$22,"Ambos")+SUMIFS('S5'!$I$6:$I$20,'S5'!$B$6:$B$20,$A20,'S5'!$E$6:$E$20,"Diego")+SUMIFS('S5'!$I$6:$I$20,'S5'!$B$6:$B$20,$A20,'S5'!$E$6:$E$20,"Ambos")+SUMIFS('S6'!$I$6:$I$17,'S6'!$B$6:$B$17,$A20,'S6'!$E$6:$E$17,"Diego")+SUMIFS('S6'!$I$6:$I$17,'S6'!$B$6:$B$17,$A20,'S6'!$E$6:$E$17,"Ambos")+SUMIFS('S7'!$I$6:$I$19,'S7'!$B$6:$B$19,$A20,'S7'!$E$6:$E$19,"Diego")+SUMIFS('S7'!$I$6:$I$19,'S7'!$B$6:$B$19,$A20,'S7'!$E$6:$E$19,"Ambos")+SUMIFS('S8'!$I$6:$I$23,'S8'!$B$6:$B$23,$A20,'S8'!$E$6:$E$23,"Diego")+SUMIFS('S8'!$I$6:$I$23,'S8'!$B$6:$B$23,$A20,'S8'!$E$6:$E$23,"Ambos")+SUMIFS('S9'!$I$6:$I$15,'S9'!$B$6:$B$15,$A20,'S9'!$E$6:$E$15,"Diego")+SUMIFS('S9'!$I$6:$I$15,'S9'!$B$6:$B$15,$A20,'S9'!$E$6:$E$15,"Ambos")+SUMIFS('S10'!$I$6:$I$13,'S10'!$B$6:$B$13,$A20,'S10'!$E$6:$E$13,"Diego")+SUMIFS('S10'!$I$6:$I$13,'S10'!$B$6:$B$13,$A20,'S10'!$E$6:$E$13,"Ambos")+SUMIFS('Holgura'!$I$6:$I$11,'Holgura'!$B$6:$B$11,$A20,'Holgura'!$E$6:$E$11,"Diego")+SUMIFS('Holgura'!$I$6:$I$11,'Holgura'!$B$6:$B$11,$A20,'Holgura'!$E$6:$E$11,"Ambos")+SUMIFS('Entrega'!$I$6:$I$9,'Entrega'!$B$6:$B$9,$A20,'Entrega'!$E$6:$E$9,"Diego")+SUMIFS('Entrega'!$I$6:$I$9,'Entrega'!$B$6:$B$9,$A20,'Entrega'!$E$6:$E$9,"Ambos")+SUMIFS('Defensa'!$I$6:$I$10,'Defensa'!$B$6:$B$10,$A20,'Defensa'!$E$6:$E$10,"Diego")+SUMIFS('Defensa'!$I$6:$I$10,'Defensa'!$B$6:$B$10,$A20,'Defensa'!$E$6:$E$10,"Ambos")</f>
         <v/>
       </c>
       <c r="F20" s="21">
-        <f>COUNTIFS('S1'!$B$6:$B$32,$A20,'S1'!$E$6:$E$32,"Víctor")+COUNTIFS('S1'!$B$6:$B$32,$A20,'S1'!$E$6:$E$32,"Ambos")+COUNTIFS('S2'!$B$6:$B$23,$A20,'S2'!$E$6:$E$23,"Víctor")+COUNTIFS('S2'!$B$6:$B$23,$A20,'S2'!$E$6:$E$23,"Ambos")+COUNTIFS('S3'!$B$6:$B$19,$A20,'S3'!$E$6:$E$19,"Víctor")+COUNTIFS('S3'!$B$6:$B$19,$A20,'S3'!$E$6:$E$19,"Ambos")+COUNTIFS('S4'!$B$6:$B$20,$A20,'S4'!$E$6:$E$20,"Víctor")+COUNTIFS('S4'!$B$6:$B$20,$A20,'S4'!$E$6:$E$20,"Ambos")+COUNTIFS('S5'!$B$6:$B$20,$A20,'S5'!$E$6:$E$20,"Víctor")+COUNTIFS('S5'!$B$6:$B$20,$A20,'S5'!$E$6:$E$20,"Ambos")+COUNTIFS('S6'!$B$6:$B$17,$A20,'S6'!$E$6:$E$17,"Víctor")+COUNTIFS('S6'!$B$6:$B$17,$A20,'S6'!$E$6:$E$17,"Ambos")+COUNTIFS('S7'!$B$6:$B$19,$A20,'S7'!$E$6:$E$19,"Víctor")+COUNTIFS('S7'!$B$6:$B$19,$A20,'S7'!$E$6:$E$19,"Ambos")+COUNTIFS('S8'!$B$6:$B$23,$A20,'S8'!$E$6:$E$23,"Víctor")+COUNTIFS('S8'!$B$6:$B$23,$A20,'S8'!$E$6:$E$23,"Ambos")+COUNTIFS('S9'!$B$6:$B$15,$A20,'S9'!$E$6:$E$15,"Víctor")+COUNTIFS('S9'!$B$6:$B$15,$A20,'S9'!$E$6:$E$15,"Ambos")+COUNTIFS('S10'!$B$6:$B$13,$A20,'S10'!$E$6:$E$13,"Víctor")+COUNTIFS('S10'!$B$6:$B$13,$A20,'S10'!$E$6:$E$13,"Ambos")+COUNTIFS('Holgura'!$B$6:$B$11,$A20,'Holgura'!$E$6:$E$11,"Víctor")+COUNTIFS('Holgura'!$B$6:$B$11,$A20,'Holgura'!$E$6:$E$11,"Ambos")+COUNTIFS('Entrega'!$B$6:$B$9,$A20,'Entrega'!$E$6:$E$9,"Víctor")+COUNTIFS('Entrega'!$B$6:$B$9,$A20,'Entrega'!$E$6:$E$9,"Ambos")+COUNTIFS('Defensa'!$B$6:$B$10,$A20,'Defensa'!$E$6:$E$10,"Víctor")+COUNTIFS('Defensa'!$B$6:$B$10,$A20,'Defensa'!$E$6:$E$10,"Ambos")</f>
+        <f>COUNTIFS('S1'!$B$6:$B$32,$A20,'S1'!$E$6:$E$32,"Víctor")+COUNTIFS('S1'!$B$6:$B$32,$A20,'S1'!$E$6:$E$32,"Ambos")+COUNTIFS('S2'!$B$6:$B$23,$A20,'S2'!$E$6:$E$23,"Víctor")+COUNTIFS('S2'!$B$6:$B$23,$A20,'S2'!$E$6:$E$23,"Ambos")+COUNTIFS('S3'!$B$6:$B$24,$A20,'S3'!$E$6:$E$24,"Víctor")+COUNTIFS('S3'!$B$6:$B$24,$A20,'S3'!$E$6:$E$24,"Ambos")+COUNTIFS('S4'!$B$6:$B$22,$A20,'S4'!$E$6:$E$22,"Víctor")+COUNTIFS('S4'!$B$6:$B$22,$A20,'S4'!$E$6:$E$22,"Ambos")+COUNTIFS('S5'!$B$6:$B$20,$A20,'S5'!$E$6:$E$20,"Víctor")+COUNTIFS('S5'!$B$6:$B$20,$A20,'S5'!$E$6:$E$20,"Ambos")+COUNTIFS('S6'!$B$6:$B$17,$A20,'S6'!$E$6:$E$17,"Víctor")+COUNTIFS('S6'!$B$6:$B$17,$A20,'S6'!$E$6:$E$17,"Ambos")+COUNTIFS('S7'!$B$6:$B$19,$A20,'S7'!$E$6:$E$19,"Víctor")+COUNTIFS('S7'!$B$6:$B$19,$A20,'S7'!$E$6:$E$19,"Ambos")+COUNTIFS('S8'!$B$6:$B$23,$A20,'S8'!$E$6:$E$23,"Víctor")+COUNTIFS('S8'!$B$6:$B$23,$A20,'S8'!$E$6:$E$23,"Ambos")+COUNTIFS('S9'!$B$6:$B$15,$A20,'S9'!$E$6:$E$15,"Víctor")+COUNTIFS('S9'!$B$6:$B$15,$A20,'S9'!$E$6:$E$15,"Ambos")+COUNTIFS('S10'!$B$6:$B$13,$A20,'S10'!$E$6:$E$13,"Víctor")+COUNTIFS('S10'!$B$6:$B$13,$A20,'S10'!$E$6:$E$13,"Ambos")+COUNTIFS('Holgura'!$B$6:$B$11,$A20,'Holgura'!$E$6:$E$11,"Víctor")+COUNTIFS('Holgura'!$B$6:$B$11,$A20,'Holgura'!$E$6:$E$11,"Ambos")+COUNTIFS('Entrega'!$B$6:$B$9,$A20,'Entrega'!$E$6:$E$9,"Víctor")+COUNTIFS('Entrega'!$B$6:$B$9,$A20,'Entrega'!$E$6:$E$9,"Ambos")+COUNTIFS('Defensa'!$B$6:$B$10,$A20,'Defensa'!$E$6:$E$10,"Víctor")+COUNTIFS('Defensa'!$B$6:$B$10,$A20,'Defensa'!$E$6:$E$10,"Ambos")</f>
         <v/>
       </c>
       <c r="G20" s="21">
-        <f>COUNTIFS('S1'!$B$6:$B$32,$A20,'S1'!$E$6:$E$32,"Diego")+COUNTIFS('S1'!$B$6:$B$32,$A20,'S1'!$E$6:$E$32,"Ambos")+COUNTIFS('S2'!$B$6:$B$23,$A20,'S2'!$E$6:$E$23,"Diego")+COUNTIFS('S2'!$B$6:$B$23,$A20,'S2'!$E$6:$E$23,"Ambos")+COUNTIFS('S3'!$B$6:$B$19,$A20,'S3'!$E$6:$E$19,"Diego")+COUNTIFS('S3'!$B$6:$B$19,$A20,'S3'!$E$6:$E$19,"Ambos")+COUNTIFS('S4'!$B$6:$B$20,$A20,'S4'!$E$6:$E$20,"Diego")+COUNTIFS('S4'!$B$6:$B$20,$A20,'S4'!$E$6:$E$20,"Ambos")+COUNTIFS('S5'!$B$6:$B$20,$A20,'S5'!$E$6:$E$20,"Diego")+COUNTIFS('S5'!$B$6:$B$20,$A20,'S5'!$E$6:$E$20,"Ambos")+COUNTIFS('S6'!$B$6:$B$17,$A20,'S6'!$E$6:$E$17,"Diego")+COUNTIFS('S6'!$B$6:$B$17,$A20,'S6'!$E$6:$E$17,"Ambos")+COUNTIFS('S7'!$B$6:$B$19,$A20,'S7'!$E$6:$E$19,"Diego")+COUNTIFS('S7'!$B$6:$B$19,$A20,'S7'!$E$6:$E$19,"Ambos")+COUNTIFS('S8'!$B$6:$B$23,$A20,'S8'!$E$6:$E$23,"Diego")+COUNTIFS('S8'!$B$6:$B$23,$A20,'S8'!$E$6:$E$23,"Ambos")+COUNTIFS('S9'!$B$6:$B$15,$A20,'S9'!$E$6:$E$15,"Diego")+COUNTIFS('S9'!$B$6:$B$15,$A20,'S9'!$E$6:$E$15,"Ambos")+COUNTIFS('S10'!$B$6:$B$13,$A20,'S10'!$E$6:$E$13,"Diego")+COUNTIFS('S10'!$B$6:$B$13,$A20,'S10'!$E$6:$E$13,"Ambos")+COUNTIFS('Holgura'!$B$6:$B$11,$A20,'Holgura'!$E$6:$E$11,"Diego")+COUNTIFS('Holgura'!$B$6:$B$11,$A20,'Holgura'!$E$6:$E$11,"Ambos")+COUNTIFS('Entrega'!$B$6:$B$9,$A20,'Entrega'!$E$6:$E$9,"Diego")+COUNTIFS('Entrega'!$B$6:$B$9,$A20,'Entrega'!$E$6:$E$9,"Ambos")+COUNTIFS('Defensa'!$B$6:$B$10,$A20,'Defensa'!$E$6:$E$10,"Diego")+COUNTIFS('Defensa'!$B$6:$B$10,$A20,'Defensa'!$E$6:$E$10,"Ambos")</f>
+        <f>COUNTIFS('S1'!$B$6:$B$32,$A20,'S1'!$E$6:$E$32,"Diego")+COUNTIFS('S1'!$B$6:$B$32,$A20,'S1'!$E$6:$E$32,"Ambos")+COUNTIFS('S2'!$B$6:$B$23,$A20,'S2'!$E$6:$E$23,"Diego")+COUNTIFS('S2'!$B$6:$B$23,$A20,'S2'!$E$6:$E$23,"Ambos")+COUNTIFS('S3'!$B$6:$B$24,$A20,'S3'!$E$6:$E$24,"Diego")+COUNTIFS('S3'!$B$6:$B$24,$A20,'S3'!$E$6:$E$24,"Ambos")+COUNTIFS('S4'!$B$6:$B$22,$A20,'S4'!$E$6:$E$22,"Diego")+COUNTIFS('S4'!$B$6:$B$22,$A20,'S4'!$E$6:$E$22,"Ambos")+COUNTIFS('S5'!$B$6:$B$20,$A20,'S5'!$E$6:$E$20,"Diego")+COUNTIFS('S5'!$B$6:$B$20,$A20,'S5'!$E$6:$E$20,"Ambos")+COUNTIFS('S6'!$B$6:$B$17,$A20,'S6'!$E$6:$E$17,"Diego")+COUNTIFS('S6'!$B$6:$B$17,$A20,'S6'!$E$6:$E$17,"Ambos")+COUNTIFS('S7'!$B$6:$B$19,$A20,'S7'!$E$6:$E$19,"Diego")+COUNTIFS('S7'!$B$6:$B$19,$A20,'S7'!$E$6:$E$19,"Ambos")+COUNTIFS('S8'!$B$6:$B$23,$A20,'S8'!$E$6:$E$23,"Diego")+COUNTIFS('S8'!$B$6:$B$23,$A20,'S8'!$E$6:$E$23,"Ambos")+COUNTIFS('S9'!$B$6:$B$15,$A20,'S9'!$E$6:$E$15,"Diego")+COUNTIFS('S9'!$B$6:$B$15,$A20,'S9'!$E$6:$E$15,"Ambos")+COUNTIFS('S10'!$B$6:$B$13,$A20,'S10'!$E$6:$E$13,"Diego")+COUNTIFS('S10'!$B$6:$B$13,$A20,'S10'!$E$6:$E$13,"Ambos")+COUNTIFS('Holgura'!$B$6:$B$11,$A20,'Holgura'!$E$6:$E$11,"Diego")+COUNTIFS('Holgura'!$B$6:$B$11,$A20,'Holgura'!$E$6:$E$11,"Ambos")+COUNTIFS('Entrega'!$B$6:$B$9,$A20,'Entrega'!$E$6:$E$9,"Diego")+COUNTIFS('Entrega'!$B$6:$B$9,$A20,'Entrega'!$E$6:$E$9,"Ambos")+COUNTIFS('Defensa'!$B$6:$B$10,$A20,'Defensa'!$E$6:$E$10,"Diego")+COUNTIFS('Defensa'!$B$6:$B$10,$A20,'Defensa'!$E$6:$E$10,"Ambos")</f>
         <v/>
       </c>
     </row>
@@ -9144,19 +9165,19 @@
         <v/>
       </c>
       <c r="D21" s="21">
-        <f>SUMIFS('S1'!$I$6:$I$32,'S1'!$B$6:$B$32,$A21,'S1'!$E$6:$E$32,"Víctor")+SUMIFS('S1'!$I$6:$I$32,'S1'!$B$6:$B$32,$A21,'S1'!$E$6:$E$32,"Ambos")+SUMIFS('S2'!$I$6:$I$23,'S2'!$B$6:$B$23,$A21,'S2'!$E$6:$E$23,"Víctor")+SUMIFS('S2'!$I$6:$I$23,'S2'!$B$6:$B$23,$A21,'S2'!$E$6:$E$23,"Ambos")+SUMIFS('S3'!$I$6:$I$19,'S3'!$B$6:$B$19,$A21,'S3'!$E$6:$E$19,"Víctor")+SUMIFS('S3'!$I$6:$I$19,'S3'!$B$6:$B$19,$A21,'S3'!$E$6:$E$19,"Ambos")+SUMIFS('S4'!$I$6:$I$20,'S4'!$B$6:$B$20,$A21,'S4'!$E$6:$E$20,"Víctor")+SUMIFS('S4'!$I$6:$I$20,'S4'!$B$6:$B$20,$A21,'S4'!$E$6:$E$20,"Ambos")+SUMIFS('S5'!$I$6:$I$20,'S5'!$B$6:$B$20,$A21,'S5'!$E$6:$E$20,"Víctor")+SUMIFS('S5'!$I$6:$I$20,'S5'!$B$6:$B$20,$A21,'S5'!$E$6:$E$20,"Ambos")+SUMIFS('S6'!$I$6:$I$17,'S6'!$B$6:$B$17,$A21,'S6'!$E$6:$E$17,"Víctor")+SUMIFS('S6'!$I$6:$I$17,'S6'!$B$6:$B$17,$A21,'S6'!$E$6:$E$17,"Ambos")+SUMIFS('S7'!$I$6:$I$19,'S7'!$B$6:$B$19,$A21,'S7'!$E$6:$E$19,"Víctor")+SUMIFS('S7'!$I$6:$I$19,'S7'!$B$6:$B$19,$A21,'S7'!$E$6:$E$19,"Ambos")+SUMIFS('S8'!$I$6:$I$23,'S8'!$B$6:$B$23,$A21,'S8'!$E$6:$E$23,"Víctor")+SUMIFS('S8'!$I$6:$I$23,'S8'!$B$6:$B$23,$A21,'S8'!$E$6:$E$23,"Ambos")+SUMIFS('S9'!$I$6:$I$15,'S9'!$B$6:$B$15,$A21,'S9'!$E$6:$E$15,"Víctor")+SUMIFS('S9'!$I$6:$I$15,'S9'!$B$6:$B$15,$A21,'S9'!$E$6:$E$15,"Ambos")+SUMIFS('S10'!$I$6:$I$13,'S10'!$B$6:$B$13,$A21,'S10'!$E$6:$E$13,"Víctor")+SUMIFS('S10'!$I$6:$I$13,'S10'!$B$6:$B$13,$A21,'S10'!$E$6:$E$13,"Ambos")+SUMIFS('Holgura'!$I$6:$I$11,'Holgura'!$B$6:$B$11,$A21,'Holgura'!$E$6:$E$11,"Víctor")+SUMIFS('Holgura'!$I$6:$I$11,'Holgura'!$B$6:$B$11,$A21,'Holgura'!$E$6:$E$11,"Ambos")+SUMIFS('Entrega'!$I$6:$I$9,'Entrega'!$B$6:$B$9,$A21,'Entrega'!$E$6:$E$9,"Víctor")+SUMIFS('Entrega'!$I$6:$I$9,'Entrega'!$B$6:$B$9,$A21,'Entrega'!$E$6:$E$9,"Ambos")+SUMIFS('Defensa'!$I$6:$I$10,'Defensa'!$B$6:$B$10,$A21,'Defensa'!$E$6:$E$10,"Víctor")+SUMIFS('Defensa'!$I$6:$I$10,'Defensa'!$B$6:$B$10,$A21,'Defensa'!$E$6:$E$10,"Ambos")</f>
+        <f>SUMIFS('S1'!$I$6:$I$32,'S1'!$B$6:$B$32,$A21,'S1'!$E$6:$E$32,"Víctor")+SUMIFS('S1'!$I$6:$I$32,'S1'!$B$6:$B$32,$A21,'S1'!$E$6:$E$32,"Ambos")+SUMIFS('S2'!$I$6:$I$23,'S2'!$B$6:$B$23,$A21,'S2'!$E$6:$E$23,"Víctor")+SUMIFS('S2'!$I$6:$I$23,'S2'!$B$6:$B$23,$A21,'S2'!$E$6:$E$23,"Ambos")+SUMIFS('S3'!$I$6:$I$24,'S3'!$B$6:$B$24,$A21,'S3'!$E$6:$E$24,"Víctor")+SUMIFS('S3'!$I$6:$I$24,'S3'!$B$6:$B$24,$A21,'S3'!$E$6:$E$24,"Ambos")+SUMIFS('S4'!$I$6:$I$22,'S4'!$B$6:$B$22,$A21,'S4'!$E$6:$E$22,"Víctor")+SUMIFS('S4'!$I$6:$I$22,'S4'!$B$6:$B$22,$A21,'S4'!$E$6:$E$22,"Ambos")+SUMIFS('S5'!$I$6:$I$20,'S5'!$B$6:$B$20,$A21,'S5'!$E$6:$E$20,"Víctor")+SUMIFS('S5'!$I$6:$I$20,'S5'!$B$6:$B$20,$A21,'S5'!$E$6:$E$20,"Ambos")+SUMIFS('S6'!$I$6:$I$17,'S6'!$B$6:$B$17,$A21,'S6'!$E$6:$E$17,"Víctor")+SUMIFS('S6'!$I$6:$I$17,'S6'!$B$6:$B$17,$A21,'S6'!$E$6:$E$17,"Ambos")+SUMIFS('S7'!$I$6:$I$19,'S7'!$B$6:$B$19,$A21,'S7'!$E$6:$E$19,"Víctor")+SUMIFS('S7'!$I$6:$I$19,'S7'!$B$6:$B$19,$A21,'S7'!$E$6:$E$19,"Ambos")+SUMIFS('S8'!$I$6:$I$23,'S8'!$B$6:$B$23,$A21,'S8'!$E$6:$E$23,"Víctor")+SUMIFS('S8'!$I$6:$I$23,'S8'!$B$6:$B$23,$A21,'S8'!$E$6:$E$23,"Ambos")+SUMIFS('S9'!$I$6:$I$15,'S9'!$B$6:$B$15,$A21,'S9'!$E$6:$E$15,"Víctor")+SUMIFS('S9'!$I$6:$I$15,'S9'!$B$6:$B$15,$A21,'S9'!$E$6:$E$15,"Ambos")+SUMIFS('S10'!$I$6:$I$13,'S10'!$B$6:$B$13,$A21,'S10'!$E$6:$E$13,"Víctor")+SUMIFS('S10'!$I$6:$I$13,'S10'!$B$6:$B$13,$A21,'S10'!$E$6:$E$13,"Ambos")+SUMIFS('Holgura'!$I$6:$I$11,'Holgura'!$B$6:$B$11,$A21,'Holgura'!$E$6:$E$11,"Víctor")+SUMIFS('Holgura'!$I$6:$I$11,'Holgura'!$B$6:$B$11,$A21,'Holgura'!$E$6:$E$11,"Ambos")+SUMIFS('Entrega'!$I$6:$I$9,'Entrega'!$B$6:$B$9,$A21,'Entrega'!$E$6:$E$9,"Víctor")+SUMIFS('Entrega'!$I$6:$I$9,'Entrega'!$B$6:$B$9,$A21,'Entrega'!$E$6:$E$9,"Ambos")+SUMIFS('Defensa'!$I$6:$I$10,'Defensa'!$B$6:$B$10,$A21,'Defensa'!$E$6:$E$10,"Víctor")+SUMIFS('Defensa'!$I$6:$I$10,'Defensa'!$B$6:$B$10,$A21,'Defensa'!$E$6:$E$10,"Ambos")</f>
         <v/>
       </c>
       <c r="E21" s="21">
-        <f>SUMIFS('S1'!$I$6:$I$32,'S1'!$B$6:$B$32,$A21,'S1'!$E$6:$E$32,"Diego")+SUMIFS('S1'!$I$6:$I$32,'S1'!$B$6:$B$32,$A21,'S1'!$E$6:$E$32,"Ambos")+SUMIFS('S2'!$I$6:$I$23,'S2'!$B$6:$B$23,$A21,'S2'!$E$6:$E$23,"Diego")+SUMIFS('S2'!$I$6:$I$23,'S2'!$B$6:$B$23,$A21,'S2'!$E$6:$E$23,"Ambos")+SUMIFS('S3'!$I$6:$I$19,'S3'!$B$6:$B$19,$A21,'S3'!$E$6:$E$19,"Diego")+SUMIFS('S3'!$I$6:$I$19,'S3'!$B$6:$B$19,$A21,'S3'!$E$6:$E$19,"Ambos")+SUMIFS('S4'!$I$6:$I$20,'S4'!$B$6:$B$20,$A21,'S4'!$E$6:$E$20,"Diego")+SUMIFS('S4'!$I$6:$I$20,'S4'!$B$6:$B$20,$A21,'S4'!$E$6:$E$20,"Ambos")+SUMIFS('S5'!$I$6:$I$20,'S5'!$B$6:$B$20,$A21,'S5'!$E$6:$E$20,"Diego")+SUMIFS('S5'!$I$6:$I$20,'S5'!$B$6:$B$20,$A21,'S5'!$E$6:$E$20,"Ambos")+SUMIFS('S6'!$I$6:$I$17,'S6'!$B$6:$B$17,$A21,'S6'!$E$6:$E$17,"Diego")+SUMIFS('S6'!$I$6:$I$17,'S6'!$B$6:$B$17,$A21,'S6'!$E$6:$E$17,"Ambos")+SUMIFS('S7'!$I$6:$I$19,'S7'!$B$6:$B$19,$A21,'S7'!$E$6:$E$19,"Diego")+SUMIFS('S7'!$I$6:$I$19,'S7'!$B$6:$B$19,$A21,'S7'!$E$6:$E$19,"Ambos")+SUMIFS('S8'!$I$6:$I$23,'S8'!$B$6:$B$23,$A21,'S8'!$E$6:$E$23,"Diego")+SUMIFS('S8'!$I$6:$I$23,'S8'!$B$6:$B$23,$A21,'S8'!$E$6:$E$23,"Ambos")+SUMIFS('S9'!$I$6:$I$15,'S9'!$B$6:$B$15,$A21,'S9'!$E$6:$E$15,"Diego")+SUMIFS('S9'!$I$6:$I$15,'S9'!$B$6:$B$15,$A21,'S9'!$E$6:$E$15,"Ambos")+SUMIFS('S10'!$I$6:$I$13,'S10'!$B$6:$B$13,$A21,'S10'!$E$6:$E$13,"Diego")+SUMIFS('S10'!$I$6:$I$13,'S10'!$B$6:$B$13,$A21,'S10'!$E$6:$E$13,"Ambos")+SUMIFS('Holgura'!$I$6:$I$11,'Holgura'!$B$6:$B$11,$A21,'Holgura'!$E$6:$E$11,"Diego")+SUMIFS('Holgura'!$I$6:$I$11,'Holgura'!$B$6:$B$11,$A21,'Holgura'!$E$6:$E$11,"Ambos")+SUMIFS('Entrega'!$I$6:$I$9,'Entrega'!$B$6:$B$9,$A21,'Entrega'!$E$6:$E$9,"Diego")+SUMIFS('Entrega'!$I$6:$I$9,'Entrega'!$B$6:$B$9,$A21,'Entrega'!$E$6:$E$9,"Ambos")+SUMIFS('Defensa'!$I$6:$I$10,'Defensa'!$B$6:$B$10,$A21,'Defensa'!$E$6:$E$10,"Diego")+SUMIFS('Defensa'!$I$6:$I$10,'Defensa'!$B$6:$B$10,$A21,'Defensa'!$E$6:$E$10,"Ambos")</f>
+        <f>SUMIFS('S1'!$I$6:$I$32,'S1'!$B$6:$B$32,$A21,'S1'!$E$6:$E$32,"Diego")+SUMIFS('S1'!$I$6:$I$32,'S1'!$B$6:$B$32,$A21,'S1'!$E$6:$E$32,"Ambos")+SUMIFS('S2'!$I$6:$I$23,'S2'!$B$6:$B$23,$A21,'S2'!$E$6:$E$23,"Diego")+SUMIFS('S2'!$I$6:$I$23,'S2'!$B$6:$B$23,$A21,'S2'!$E$6:$E$23,"Ambos")+SUMIFS('S3'!$I$6:$I$24,'S3'!$B$6:$B$24,$A21,'S3'!$E$6:$E$24,"Diego")+SUMIFS('S3'!$I$6:$I$24,'S3'!$B$6:$B$24,$A21,'S3'!$E$6:$E$24,"Ambos")+SUMIFS('S4'!$I$6:$I$22,'S4'!$B$6:$B$22,$A21,'S4'!$E$6:$E$22,"Diego")+SUMIFS('S4'!$I$6:$I$22,'S4'!$B$6:$B$22,$A21,'S4'!$E$6:$E$22,"Ambos")+SUMIFS('S5'!$I$6:$I$20,'S5'!$B$6:$B$20,$A21,'S5'!$E$6:$E$20,"Diego")+SUMIFS('S5'!$I$6:$I$20,'S5'!$B$6:$B$20,$A21,'S5'!$E$6:$E$20,"Ambos")+SUMIFS('S6'!$I$6:$I$17,'S6'!$B$6:$B$17,$A21,'S6'!$E$6:$E$17,"Diego")+SUMIFS('S6'!$I$6:$I$17,'S6'!$B$6:$B$17,$A21,'S6'!$E$6:$E$17,"Ambos")+SUMIFS('S7'!$I$6:$I$19,'S7'!$B$6:$B$19,$A21,'S7'!$E$6:$E$19,"Diego")+SUMIFS('S7'!$I$6:$I$19,'S7'!$B$6:$B$19,$A21,'S7'!$E$6:$E$19,"Ambos")+SUMIFS('S8'!$I$6:$I$23,'S8'!$B$6:$B$23,$A21,'S8'!$E$6:$E$23,"Diego")+SUMIFS('S8'!$I$6:$I$23,'S8'!$B$6:$B$23,$A21,'S8'!$E$6:$E$23,"Ambos")+SUMIFS('S9'!$I$6:$I$15,'S9'!$B$6:$B$15,$A21,'S9'!$E$6:$E$15,"Diego")+SUMIFS('S9'!$I$6:$I$15,'S9'!$B$6:$B$15,$A21,'S9'!$E$6:$E$15,"Ambos")+SUMIFS('S10'!$I$6:$I$13,'S10'!$B$6:$B$13,$A21,'S10'!$E$6:$E$13,"Diego")+SUMIFS('S10'!$I$6:$I$13,'S10'!$B$6:$B$13,$A21,'S10'!$E$6:$E$13,"Ambos")+SUMIFS('Holgura'!$I$6:$I$11,'Holgura'!$B$6:$B$11,$A21,'Holgura'!$E$6:$E$11,"Diego")+SUMIFS('Holgura'!$I$6:$I$11,'Holgura'!$B$6:$B$11,$A21,'Holgura'!$E$6:$E$11,"Ambos")+SUMIFS('Entrega'!$I$6:$I$9,'Entrega'!$B$6:$B$9,$A21,'Entrega'!$E$6:$E$9,"Diego")+SUMIFS('Entrega'!$I$6:$I$9,'Entrega'!$B$6:$B$9,$A21,'Entrega'!$E$6:$E$9,"Ambos")+SUMIFS('Defensa'!$I$6:$I$10,'Defensa'!$B$6:$B$10,$A21,'Defensa'!$E$6:$E$10,"Diego")+SUMIFS('Defensa'!$I$6:$I$10,'Defensa'!$B$6:$B$10,$A21,'Defensa'!$E$6:$E$10,"Ambos")</f>
         <v/>
       </c>
       <c r="F21" s="21">
-        <f>COUNTIFS('S1'!$B$6:$B$32,$A21,'S1'!$E$6:$E$32,"Víctor")+COUNTIFS('S1'!$B$6:$B$32,$A21,'S1'!$E$6:$E$32,"Ambos")+COUNTIFS('S2'!$B$6:$B$23,$A21,'S2'!$E$6:$E$23,"Víctor")+COUNTIFS('S2'!$B$6:$B$23,$A21,'S2'!$E$6:$E$23,"Ambos")+COUNTIFS('S3'!$B$6:$B$19,$A21,'S3'!$E$6:$E$19,"Víctor")+COUNTIFS('S3'!$B$6:$B$19,$A21,'S3'!$E$6:$E$19,"Ambos")+COUNTIFS('S4'!$B$6:$B$20,$A21,'S4'!$E$6:$E$20,"Víctor")+COUNTIFS('S4'!$B$6:$B$20,$A21,'S4'!$E$6:$E$20,"Ambos")+COUNTIFS('S5'!$B$6:$B$20,$A21,'S5'!$E$6:$E$20,"Víctor")+COUNTIFS('S5'!$B$6:$B$20,$A21,'S5'!$E$6:$E$20,"Ambos")+COUNTIFS('S6'!$B$6:$B$17,$A21,'S6'!$E$6:$E$17,"Víctor")+COUNTIFS('S6'!$B$6:$B$17,$A21,'S6'!$E$6:$E$17,"Ambos")+COUNTIFS('S7'!$B$6:$B$19,$A21,'S7'!$E$6:$E$19,"Víctor")+COUNTIFS('S7'!$B$6:$B$19,$A21,'S7'!$E$6:$E$19,"Ambos")+COUNTIFS('S8'!$B$6:$B$23,$A21,'S8'!$E$6:$E$23,"Víctor")+COUNTIFS('S8'!$B$6:$B$23,$A21,'S8'!$E$6:$E$23,"Ambos")+COUNTIFS('S9'!$B$6:$B$15,$A21,'S9'!$E$6:$E$15,"Víctor")+COUNTIFS('S9'!$B$6:$B$15,$A21,'S9'!$E$6:$E$15,"Ambos")+COUNTIFS('S10'!$B$6:$B$13,$A21,'S10'!$E$6:$E$13,"Víctor")+COUNTIFS('S10'!$B$6:$B$13,$A21,'S10'!$E$6:$E$13,"Ambos")+COUNTIFS('Holgura'!$B$6:$B$11,$A21,'Holgura'!$E$6:$E$11,"Víctor")+COUNTIFS('Holgura'!$B$6:$B$11,$A21,'Holgura'!$E$6:$E$11,"Ambos")+COUNTIFS('Entrega'!$B$6:$B$9,$A21,'Entrega'!$E$6:$E$9,"Víctor")+COUNTIFS('Entrega'!$B$6:$B$9,$A21,'Entrega'!$E$6:$E$9,"Ambos")+COUNTIFS('Defensa'!$B$6:$B$10,$A21,'Defensa'!$E$6:$E$10,"Víctor")+COUNTIFS('Defensa'!$B$6:$B$10,$A21,'Defensa'!$E$6:$E$10,"Ambos")</f>
+        <f>COUNTIFS('S1'!$B$6:$B$32,$A21,'S1'!$E$6:$E$32,"Víctor")+COUNTIFS('S1'!$B$6:$B$32,$A21,'S1'!$E$6:$E$32,"Ambos")+COUNTIFS('S2'!$B$6:$B$23,$A21,'S2'!$E$6:$E$23,"Víctor")+COUNTIFS('S2'!$B$6:$B$23,$A21,'S2'!$E$6:$E$23,"Ambos")+COUNTIFS('S3'!$B$6:$B$24,$A21,'S3'!$E$6:$E$24,"Víctor")+COUNTIFS('S3'!$B$6:$B$24,$A21,'S3'!$E$6:$E$24,"Ambos")+COUNTIFS('S4'!$B$6:$B$22,$A21,'S4'!$E$6:$E$22,"Víctor")+COUNTIFS('S4'!$B$6:$B$22,$A21,'S4'!$E$6:$E$22,"Ambos")+COUNTIFS('S5'!$B$6:$B$20,$A21,'S5'!$E$6:$E$20,"Víctor")+COUNTIFS('S5'!$B$6:$B$20,$A21,'S5'!$E$6:$E$20,"Ambos")+COUNTIFS('S6'!$B$6:$B$17,$A21,'S6'!$E$6:$E$17,"Víctor")+COUNTIFS('S6'!$B$6:$B$17,$A21,'S6'!$E$6:$E$17,"Ambos")+COUNTIFS('S7'!$B$6:$B$19,$A21,'S7'!$E$6:$E$19,"Víctor")+COUNTIFS('S7'!$B$6:$B$19,$A21,'S7'!$E$6:$E$19,"Ambos")+COUNTIFS('S8'!$B$6:$B$23,$A21,'S8'!$E$6:$E$23,"Víctor")+COUNTIFS('S8'!$B$6:$B$23,$A21,'S8'!$E$6:$E$23,"Ambos")+COUNTIFS('S9'!$B$6:$B$15,$A21,'S9'!$E$6:$E$15,"Víctor")+COUNTIFS('S9'!$B$6:$B$15,$A21,'S9'!$E$6:$E$15,"Ambos")+COUNTIFS('S10'!$B$6:$B$13,$A21,'S10'!$E$6:$E$13,"Víctor")+COUNTIFS('S10'!$B$6:$B$13,$A21,'S10'!$E$6:$E$13,"Ambos")+COUNTIFS('Holgura'!$B$6:$B$11,$A21,'Holgura'!$E$6:$E$11,"Víctor")+COUNTIFS('Holgura'!$B$6:$B$11,$A21,'Holgura'!$E$6:$E$11,"Ambos")+COUNTIFS('Entrega'!$B$6:$B$9,$A21,'Entrega'!$E$6:$E$9,"Víctor")+COUNTIFS('Entrega'!$B$6:$B$9,$A21,'Entrega'!$E$6:$E$9,"Ambos")+COUNTIFS('Defensa'!$B$6:$B$10,$A21,'Defensa'!$E$6:$E$10,"Víctor")+COUNTIFS('Defensa'!$B$6:$B$10,$A21,'Defensa'!$E$6:$E$10,"Ambos")</f>
         <v/>
       </c>
       <c r="G21" s="21">
-        <f>COUNTIFS('S1'!$B$6:$B$32,$A21,'S1'!$E$6:$E$32,"Diego")+COUNTIFS('S1'!$B$6:$B$32,$A21,'S1'!$E$6:$E$32,"Ambos")+COUNTIFS('S2'!$B$6:$B$23,$A21,'S2'!$E$6:$E$23,"Diego")+COUNTIFS('S2'!$B$6:$B$23,$A21,'S2'!$E$6:$E$23,"Ambos")+COUNTIFS('S3'!$B$6:$B$19,$A21,'S3'!$E$6:$E$19,"Diego")+COUNTIFS('S3'!$B$6:$B$19,$A21,'S3'!$E$6:$E$19,"Ambos")+COUNTIFS('S4'!$B$6:$B$20,$A21,'S4'!$E$6:$E$20,"Diego")+COUNTIFS('S4'!$B$6:$B$20,$A21,'S4'!$E$6:$E$20,"Ambos")+COUNTIFS('S5'!$B$6:$B$20,$A21,'S5'!$E$6:$E$20,"Diego")+COUNTIFS('S5'!$B$6:$B$20,$A21,'S5'!$E$6:$E$20,"Ambos")+COUNTIFS('S6'!$B$6:$B$17,$A21,'S6'!$E$6:$E$17,"Diego")+COUNTIFS('S6'!$B$6:$B$17,$A21,'S6'!$E$6:$E$17,"Ambos")+COUNTIFS('S7'!$B$6:$B$19,$A21,'S7'!$E$6:$E$19,"Diego")+COUNTIFS('S7'!$B$6:$B$19,$A21,'S7'!$E$6:$E$19,"Ambos")+COUNTIFS('S8'!$B$6:$B$23,$A21,'S8'!$E$6:$E$23,"Diego")+COUNTIFS('S8'!$B$6:$B$23,$A21,'S8'!$E$6:$E$23,"Ambos")+COUNTIFS('S9'!$B$6:$B$15,$A21,'S9'!$E$6:$E$15,"Diego")+COUNTIFS('S9'!$B$6:$B$15,$A21,'S9'!$E$6:$E$15,"Ambos")+COUNTIFS('S10'!$B$6:$B$13,$A21,'S10'!$E$6:$E$13,"Diego")+COUNTIFS('S10'!$B$6:$B$13,$A21,'S10'!$E$6:$E$13,"Ambos")+COUNTIFS('Holgura'!$B$6:$B$11,$A21,'Holgura'!$E$6:$E$11,"Diego")+COUNTIFS('Holgura'!$B$6:$B$11,$A21,'Holgura'!$E$6:$E$11,"Ambos")+COUNTIFS('Entrega'!$B$6:$B$9,$A21,'Entrega'!$E$6:$E$9,"Diego")+COUNTIFS('Entrega'!$B$6:$B$9,$A21,'Entrega'!$E$6:$E$9,"Ambos")+COUNTIFS('Defensa'!$B$6:$B$10,$A21,'Defensa'!$E$6:$E$10,"Diego")+COUNTIFS('Defensa'!$B$6:$B$10,$A21,'Defensa'!$E$6:$E$10,"Ambos")</f>
+        <f>COUNTIFS('S1'!$B$6:$B$32,$A21,'S1'!$E$6:$E$32,"Diego")+COUNTIFS('S1'!$B$6:$B$32,$A21,'S1'!$E$6:$E$32,"Ambos")+COUNTIFS('S2'!$B$6:$B$23,$A21,'S2'!$E$6:$E$23,"Diego")+COUNTIFS('S2'!$B$6:$B$23,$A21,'S2'!$E$6:$E$23,"Ambos")+COUNTIFS('S3'!$B$6:$B$24,$A21,'S3'!$E$6:$E$24,"Diego")+COUNTIFS('S3'!$B$6:$B$24,$A21,'S3'!$E$6:$E$24,"Ambos")+COUNTIFS('S4'!$B$6:$B$22,$A21,'S4'!$E$6:$E$22,"Diego")+COUNTIFS('S4'!$B$6:$B$22,$A21,'S4'!$E$6:$E$22,"Ambos")+COUNTIFS('S5'!$B$6:$B$20,$A21,'S5'!$E$6:$E$20,"Diego")+COUNTIFS('S5'!$B$6:$B$20,$A21,'S5'!$E$6:$E$20,"Ambos")+COUNTIFS('S6'!$B$6:$B$17,$A21,'S6'!$E$6:$E$17,"Diego")+COUNTIFS('S6'!$B$6:$B$17,$A21,'S6'!$E$6:$E$17,"Ambos")+COUNTIFS('S7'!$B$6:$B$19,$A21,'S7'!$E$6:$E$19,"Diego")+COUNTIFS('S7'!$B$6:$B$19,$A21,'S7'!$E$6:$E$19,"Ambos")+COUNTIFS('S8'!$B$6:$B$23,$A21,'S8'!$E$6:$E$23,"Diego")+COUNTIFS('S8'!$B$6:$B$23,$A21,'S8'!$E$6:$E$23,"Ambos")+COUNTIFS('S9'!$B$6:$B$15,$A21,'S9'!$E$6:$E$15,"Diego")+COUNTIFS('S9'!$B$6:$B$15,$A21,'S9'!$E$6:$E$15,"Ambos")+COUNTIFS('S10'!$B$6:$B$13,$A21,'S10'!$E$6:$E$13,"Diego")+COUNTIFS('S10'!$B$6:$B$13,$A21,'S10'!$E$6:$E$13,"Ambos")+COUNTIFS('Holgura'!$B$6:$B$11,$A21,'Holgura'!$E$6:$E$11,"Diego")+COUNTIFS('Holgura'!$B$6:$B$11,$A21,'Holgura'!$E$6:$E$11,"Ambos")+COUNTIFS('Entrega'!$B$6:$B$9,$A21,'Entrega'!$E$6:$E$9,"Diego")+COUNTIFS('Entrega'!$B$6:$B$9,$A21,'Entrega'!$E$6:$E$9,"Ambos")+COUNTIFS('Defensa'!$B$6:$B$10,$A21,'Defensa'!$E$6:$E$10,"Diego")+COUNTIFS('Defensa'!$B$6:$B$10,$A21,'Defensa'!$E$6:$E$10,"Ambos")</f>
         <v/>
       </c>
     </row>
@@ -9173,19 +9194,19 @@
         <v/>
       </c>
       <c r="D22" s="21">
-        <f>SUMIFS('S1'!$I$6:$I$32,'S1'!$B$6:$B$32,$A22,'S1'!$E$6:$E$32,"Víctor")+SUMIFS('S1'!$I$6:$I$32,'S1'!$B$6:$B$32,$A22,'S1'!$E$6:$E$32,"Ambos")+SUMIFS('S2'!$I$6:$I$23,'S2'!$B$6:$B$23,$A22,'S2'!$E$6:$E$23,"Víctor")+SUMIFS('S2'!$I$6:$I$23,'S2'!$B$6:$B$23,$A22,'S2'!$E$6:$E$23,"Ambos")+SUMIFS('S3'!$I$6:$I$19,'S3'!$B$6:$B$19,$A22,'S3'!$E$6:$E$19,"Víctor")+SUMIFS('S3'!$I$6:$I$19,'S3'!$B$6:$B$19,$A22,'S3'!$E$6:$E$19,"Ambos")+SUMIFS('S4'!$I$6:$I$20,'S4'!$B$6:$B$20,$A22,'S4'!$E$6:$E$20,"Víctor")+SUMIFS('S4'!$I$6:$I$20,'S4'!$B$6:$B$20,$A22,'S4'!$E$6:$E$20,"Ambos")+SUMIFS('S5'!$I$6:$I$20,'S5'!$B$6:$B$20,$A22,'S5'!$E$6:$E$20,"Víctor")+SUMIFS('S5'!$I$6:$I$20,'S5'!$B$6:$B$20,$A22,'S5'!$E$6:$E$20,"Ambos")+SUMIFS('S6'!$I$6:$I$17,'S6'!$B$6:$B$17,$A22,'S6'!$E$6:$E$17,"Víctor")+SUMIFS('S6'!$I$6:$I$17,'S6'!$B$6:$B$17,$A22,'S6'!$E$6:$E$17,"Ambos")+SUMIFS('S7'!$I$6:$I$19,'S7'!$B$6:$B$19,$A22,'S7'!$E$6:$E$19,"Víctor")+SUMIFS('S7'!$I$6:$I$19,'S7'!$B$6:$B$19,$A22,'S7'!$E$6:$E$19,"Ambos")+SUMIFS('S8'!$I$6:$I$23,'S8'!$B$6:$B$23,$A22,'S8'!$E$6:$E$23,"Víctor")+SUMIFS('S8'!$I$6:$I$23,'S8'!$B$6:$B$23,$A22,'S8'!$E$6:$E$23,"Ambos")+SUMIFS('S9'!$I$6:$I$15,'S9'!$B$6:$B$15,$A22,'S9'!$E$6:$E$15,"Víctor")+SUMIFS('S9'!$I$6:$I$15,'S9'!$B$6:$B$15,$A22,'S9'!$E$6:$E$15,"Ambos")+SUMIFS('S10'!$I$6:$I$13,'S10'!$B$6:$B$13,$A22,'S10'!$E$6:$E$13,"Víctor")+SUMIFS('S10'!$I$6:$I$13,'S10'!$B$6:$B$13,$A22,'S10'!$E$6:$E$13,"Ambos")+SUMIFS('Holgura'!$I$6:$I$11,'Holgura'!$B$6:$B$11,$A22,'Holgura'!$E$6:$E$11,"Víctor")+SUMIFS('Holgura'!$I$6:$I$11,'Holgura'!$B$6:$B$11,$A22,'Holgura'!$E$6:$E$11,"Ambos")+SUMIFS('Entrega'!$I$6:$I$9,'Entrega'!$B$6:$B$9,$A22,'Entrega'!$E$6:$E$9,"Víctor")+SUMIFS('Entrega'!$I$6:$I$9,'Entrega'!$B$6:$B$9,$A22,'Entrega'!$E$6:$E$9,"Ambos")+SUMIFS('Defensa'!$I$6:$I$10,'Defensa'!$B$6:$B$10,$A22,'Defensa'!$E$6:$E$10,"Víctor")+SUMIFS('Defensa'!$I$6:$I$10,'Defensa'!$B$6:$B$10,$A22,'Defensa'!$E$6:$E$10,"Ambos")</f>
+        <f>SUMIFS('S1'!$I$6:$I$32,'S1'!$B$6:$B$32,$A22,'S1'!$E$6:$E$32,"Víctor")+SUMIFS('S1'!$I$6:$I$32,'S1'!$B$6:$B$32,$A22,'S1'!$E$6:$E$32,"Ambos")+SUMIFS('S2'!$I$6:$I$23,'S2'!$B$6:$B$23,$A22,'S2'!$E$6:$E$23,"Víctor")+SUMIFS('S2'!$I$6:$I$23,'S2'!$B$6:$B$23,$A22,'S2'!$E$6:$E$23,"Ambos")+SUMIFS('S3'!$I$6:$I$24,'S3'!$B$6:$B$24,$A22,'S3'!$E$6:$E$24,"Víctor")+SUMIFS('S3'!$I$6:$I$24,'S3'!$B$6:$B$24,$A22,'S3'!$E$6:$E$24,"Ambos")+SUMIFS('S4'!$I$6:$I$22,'S4'!$B$6:$B$22,$A22,'S4'!$E$6:$E$22,"Víctor")+SUMIFS('S4'!$I$6:$I$22,'S4'!$B$6:$B$22,$A22,'S4'!$E$6:$E$22,"Ambos")+SUMIFS('S5'!$I$6:$I$20,'S5'!$B$6:$B$20,$A22,'S5'!$E$6:$E$20,"Víctor")+SUMIFS('S5'!$I$6:$I$20,'S5'!$B$6:$B$20,$A22,'S5'!$E$6:$E$20,"Ambos")+SUMIFS('S6'!$I$6:$I$17,'S6'!$B$6:$B$17,$A22,'S6'!$E$6:$E$17,"Víctor")+SUMIFS('S6'!$I$6:$I$17,'S6'!$B$6:$B$17,$A22,'S6'!$E$6:$E$17,"Ambos")+SUMIFS('S7'!$I$6:$I$19,'S7'!$B$6:$B$19,$A22,'S7'!$E$6:$E$19,"Víctor")+SUMIFS('S7'!$I$6:$I$19,'S7'!$B$6:$B$19,$A22,'S7'!$E$6:$E$19,"Ambos")+SUMIFS('S8'!$I$6:$I$23,'S8'!$B$6:$B$23,$A22,'S8'!$E$6:$E$23,"Víctor")+SUMIFS('S8'!$I$6:$I$23,'S8'!$B$6:$B$23,$A22,'S8'!$E$6:$E$23,"Ambos")+SUMIFS('S9'!$I$6:$I$15,'S9'!$B$6:$B$15,$A22,'S9'!$E$6:$E$15,"Víctor")+SUMIFS('S9'!$I$6:$I$15,'S9'!$B$6:$B$15,$A22,'S9'!$E$6:$E$15,"Ambos")+SUMIFS('S10'!$I$6:$I$13,'S10'!$B$6:$B$13,$A22,'S10'!$E$6:$E$13,"Víctor")+SUMIFS('S10'!$I$6:$I$13,'S10'!$B$6:$B$13,$A22,'S10'!$E$6:$E$13,"Ambos")+SUMIFS('Holgura'!$I$6:$I$11,'Holgura'!$B$6:$B$11,$A22,'Holgura'!$E$6:$E$11,"Víctor")+SUMIFS('Holgura'!$I$6:$I$11,'Holgura'!$B$6:$B$11,$A22,'Holgura'!$E$6:$E$11,"Ambos")+SUMIFS('Entrega'!$I$6:$I$9,'Entrega'!$B$6:$B$9,$A22,'Entrega'!$E$6:$E$9,"Víctor")+SUMIFS('Entrega'!$I$6:$I$9,'Entrega'!$B$6:$B$9,$A22,'Entrega'!$E$6:$E$9,"Ambos")+SUMIFS('Defensa'!$I$6:$I$10,'Defensa'!$B$6:$B$10,$A22,'Defensa'!$E$6:$E$10,"Víctor")+SUMIFS('Defensa'!$I$6:$I$10,'Defensa'!$B$6:$B$10,$A22,'Defensa'!$E$6:$E$10,"Ambos")</f>
         <v/>
       </c>
       <c r="E22" s="21">
-        <f>SUMIFS('S1'!$I$6:$I$32,'S1'!$B$6:$B$32,$A22,'S1'!$E$6:$E$32,"Diego")+SUMIFS('S1'!$I$6:$I$32,'S1'!$B$6:$B$32,$A22,'S1'!$E$6:$E$32,"Ambos")+SUMIFS('S2'!$I$6:$I$23,'S2'!$B$6:$B$23,$A22,'S2'!$E$6:$E$23,"Diego")+SUMIFS('S2'!$I$6:$I$23,'S2'!$B$6:$B$23,$A22,'S2'!$E$6:$E$23,"Ambos")+SUMIFS('S3'!$I$6:$I$19,'S3'!$B$6:$B$19,$A22,'S3'!$E$6:$E$19,"Diego")+SUMIFS('S3'!$I$6:$I$19,'S3'!$B$6:$B$19,$A22,'S3'!$E$6:$E$19,"Ambos")+SUMIFS('S4'!$I$6:$I$20,'S4'!$B$6:$B$20,$A22,'S4'!$E$6:$E$20,"Diego")+SUMIFS('S4'!$I$6:$I$20,'S4'!$B$6:$B$20,$A22,'S4'!$E$6:$E$20,"Ambos")+SUMIFS('S5'!$I$6:$I$20,'S5'!$B$6:$B$20,$A22,'S5'!$E$6:$E$20,"Diego")+SUMIFS('S5'!$I$6:$I$20,'S5'!$B$6:$B$20,$A22,'S5'!$E$6:$E$20,"Ambos")+SUMIFS('S6'!$I$6:$I$17,'S6'!$B$6:$B$17,$A22,'S6'!$E$6:$E$17,"Diego")+SUMIFS('S6'!$I$6:$I$17,'S6'!$B$6:$B$17,$A22,'S6'!$E$6:$E$17,"Ambos")+SUMIFS('S7'!$I$6:$I$19,'S7'!$B$6:$B$19,$A22,'S7'!$E$6:$E$19,"Diego")+SUMIFS('S7'!$I$6:$I$19,'S7'!$B$6:$B$19,$A22,'S7'!$E$6:$E$19,"Ambos")+SUMIFS('S8'!$I$6:$I$23,'S8'!$B$6:$B$23,$A22,'S8'!$E$6:$E$23,"Diego")+SUMIFS('S8'!$I$6:$I$23,'S8'!$B$6:$B$23,$A22,'S8'!$E$6:$E$23,"Ambos")+SUMIFS('S9'!$I$6:$I$15,'S9'!$B$6:$B$15,$A22,'S9'!$E$6:$E$15,"Diego")+SUMIFS('S9'!$I$6:$I$15,'S9'!$B$6:$B$15,$A22,'S9'!$E$6:$E$15,"Ambos")+SUMIFS('S10'!$I$6:$I$13,'S10'!$B$6:$B$13,$A22,'S10'!$E$6:$E$13,"Diego")+SUMIFS('S10'!$I$6:$I$13,'S10'!$B$6:$B$13,$A22,'S10'!$E$6:$E$13,"Ambos")+SUMIFS('Holgura'!$I$6:$I$11,'Holgura'!$B$6:$B$11,$A22,'Holgura'!$E$6:$E$11,"Diego")+SUMIFS('Holgura'!$I$6:$I$11,'Holgura'!$B$6:$B$11,$A22,'Holgura'!$E$6:$E$11,"Ambos")+SUMIFS('Entrega'!$I$6:$I$9,'Entrega'!$B$6:$B$9,$A22,'Entrega'!$E$6:$E$9,"Diego")+SUMIFS('Entrega'!$I$6:$I$9,'Entrega'!$B$6:$B$9,$A22,'Entrega'!$E$6:$E$9,"Ambos")+SUMIFS('Defensa'!$I$6:$I$10,'Defensa'!$B$6:$B$10,$A22,'Defensa'!$E$6:$E$10,"Diego")+SUMIFS('Defensa'!$I$6:$I$10,'Defensa'!$B$6:$B$10,$A22,'Defensa'!$E$6:$E$10,"Ambos")</f>
+        <f>SUMIFS('S1'!$I$6:$I$32,'S1'!$B$6:$B$32,$A22,'S1'!$E$6:$E$32,"Diego")+SUMIFS('S1'!$I$6:$I$32,'S1'!$B$6:$B$32,$A22,'S1'!$E$6:$E$32,"Ambos")+SUMIFS('S2'!$I$6:$I$23,'S2'!$B$6:$B$23,$A22,'S2'!$E$6:$E$23,"Diego")+SUMIFS('S2'!$I$6:$I$23,'S2'!$B$6:$B$23,$A22,'S2'!$E$6:$E$23,"Ambos")+SUMIFS('S3'!$I$6:$I$24,'S3'!$B$6:$B$24,$A22,'S3'!$E$6:$E$24,"Diego")+SUMIFS('S3'!$I$6:$I$24,'S3'!$B$6:$B$24,$A22,'S3'!$E$6:$E$24,"Ambos")+SUMIFS('S4'!$I$6:$I$22,'S4'!$B$6:$B$22,$A22,'S4'!$E$6:$E$22,"Diego")+SUMIFS('S4'!$I$6:$I$22,'S4'!$B$6:$B$22,$A22,'S4'!$E$6:$E$22,"Ambos")+SUMIFS('S5'!$I$6:$I$20,'S5'!$B$6:$B$20,$A22,'S5'!$E$6:$E$20,"Diego")+SUMIFS('S5'!$I$6:$I$20,'S5'!$B$6:$B$20,$A22,'S5'!$E$6:$E$20,"Ambos")+SUMIFS('S6'!$I$6:$I$17,'S6'!$B$6:$B$17,$A22,'S6'!$E$6:$E$17,"Diego")+SUMIFS('S6'!$I$6:$I$17,'S6'!$B$6:$B$17,$A22,'S6'!$E$6:$E$17,"Ambos")+SUMIFS('S7'!$I$6:$I$19,'S7'!$B$6:$B$19,$A22,'S7'!$E$6:$E$19,"Diego")+SUMIFS('S7'!$I$6:$I$19,'S7'!$B$6:$B$19,$A22,'S7'!$E$6:$E$19,"Ambos")+SUMIFS('S8'!$I$6:$I$23,'S8'!$B$6:$B$23,$A22,'S8'!$E$6:$E$23,"Diego")+SUMIFS('S8'!$I$6:$I$23,'S8'!$B$6:$B$23,$A22,'S8'!$E$6:$E$23,"Ambos")+SUMIFS('S9'!$I$6:$I$15,'S9'!$B$6:$B$15,$A22,'S9'!$E$6:$E$15,"Diego")+SUMIFS('S9'!$I$6:$I$15,'S9'!$B$6:$B$15,$A22,'S9'!$E$6:$E$15,"Ambos")+SUMIFS('S10'!$I$6:$I$13,'S10'!$B$6:$B$13,$A22,'S10'!$E$6:$E$13,"Diego")+SUMIFS('S10'!$I$6:$I$13,'S10'!$B$6:$B$13,$A22,'S10'!$E$6:$E$13,"Ambos")+SUMIFS('Holgura'!$I$6:$I$11,'Holgura'!$B$6:$B$11,$A22,'Holgura'!$E$6:$E$11,"Diego")+SUMIFS('Holgura'!$I$6:$I$11,'Holgura'!$B$6:$B$11,$A22,'Holgura'!$E$6:$E$11,"Ambos")+SUMIFS('Entrega'!$I$6:$I$9,'Entrega'!$B$6:$B$9,$A22,'Entrega'!$E$6:$E$9,"Diego")+SUMIFS('Entrega'!$I$6:$I$9,'Entrega'!$B$6:$B$9,$A22,'Entrega'!$E$6:$E$9,"Ambos")+SUMIFS('Defensa'!$I$6:$I$10,'Defensa'!$B$6:$B$10,$A22,'Defensa'!$E$6:$E$10,"Diego")+SUMIFS('Defensa'!$I$6:$I$10,'Defensa'!$B$6:$B$10,$A22,'Defensa'!$E$6:$E$10,"Ambos")</f>
         <v/>
       </c>
       <c r="F22" s="21">
-        <f>COUNTIFS('S1'!$B$6:$B$32,$A22,'S1'!$E$6:$E$32,"Víctor")+COUNTIFS('S1'!$B$6:$B$32,$A22,'S1'!$E$6:$E$32,"Ambos")+COUNTIFS('S2'!$B$6:$B$23,$A22,'S2'!$E$6:$E$23,"Víctor")+COUNTIFS('S2'!$B$6:$B$23,$A22,'S2'!$E$6:$E$23,"Ambos")+COUNTIFS('S3'!$B$6:$B$19,$A22,'S3'!$E$6:$E$19,"Víctor")+COUNTIFS('S3'!$B$6:$B$19,$A22,'S3'!$E$6:$E$19,"Ambos")+COUNTIFS('S4'!$B$6:$B$20,$A22,'S4'!$E$6:$E$20,"Víctor")+COUNTIFS('S4'!$B$6:$B$20,$A22,'S4'!$E$6:$E$20,"Ambos")+COUNTIFS('S5'!$B$6:$B$20,$A22,'S5'!$E$6:$E$20,"Víctor")+COUNTIFS('S5'!$B$6:$B$20,$A22,'S5'!$E$6:$E$20,"Ambos")+COUNTIFS('S6'!$B$6:$B$17,$A22,'S6'!$E$6:$E$17,"Víctor")+COUNTIFS('S6'!$B$6:$B$17,$A22,'S6'!$E$6:$E$17,"Ambos")+COUNTIFS('S7'!$B$6:$B$19,$A22,'S7'!$E$6:$E$19,"Víctor")+COUNTIFS('S7'!$B$6:$B$19,$A22,'S7'!$E$6:$E$19,"Ambos")+COUNTIFS('S8'!$B$6:$B$23,$A22,'S8'!$E$6:$E$23,"Víctor")+COUNTIFS('S8'!$B$6:$B$23,$A22,'S8'!$E$6:$E$23,"Ambos")+COUNTIFS('S9'!$B$6:$B$15,$A22,'S9'!$E$6:$E$15,"Víctor")+COUNTIFS('S9'!$B$6:$B$15,$A22,'S9'!$E$6:$E$15,"Ambos")+COUNTIFS('S10'!$B$6:$B$13,$A22,'S10'!$E$6:$E$13,"Víctor")+COUNTIFS('S10'!$B$6:$B$13,$A22,'S10'!$E$6:$E$13,"Ambos")+COUNTIFS('Holgura'!$B$6:$B$11,$A22,'Holgura'!$E$6:$E$11,"Víctor")+COUNTIFS('Holgura'!$B$6:$B$11,$A22,'Holgura'!$E$6:$E$11,"Ambos")+COUNTIFS('Entrega'!$B$6:$B$9,$A22,'Entrega'!$E$6:$E$9,"Víctor")+COUNTIFS('Entrega'!$B$6:$B$9,$A22,'Entrega'!$E$6:$E$9,"Ambos")+COUNTIFS('Defensa'!$B$6:$B$10,$A22,'Defensa'!$E$6:$E$10,"Víctor")+COUNTIFS('Defensa'!$B$6:$B$10,$A22,'Defensa'!$E$6:$E$10,"Ambos")</f>
+        <f>COUNTIFS('S1'!$B$6:$B$32,$A22,'S1'!$E$6:$E$32,"Víctor")+COUNTIFS('S1'!$B$6:$B$32,$A22,'S1'!$E$6:$E$32,"Ambos")+COUNTIFS('S2'!$B$6:$B$23,$A22,'S2'!$E$6:$E$23,"Víctor")+COUNTIFS('S2'!$B$6:$B$23,$A22,'S2'!$E$6:$E$23,"Ambos")+COUNTIFS('S3'!$B$6:$B$24,$A22,'S3'!$E$6:$E$24,"Víctor")+COUNTIFS('S3'!$B$6:$B$24,$A22,'S3'!$E$6:$E$24,"Ambos")+COUNTIFS('S4'!$B$6:$B$22,$A22,'S4'!$E$6:$E$22,"Víctor")+COUNTIFS('S4'!$B$6:$B$22,$A22,'S4'!$E$6:$E$22,"Ambos")+COUNTIFS('S5'!$B$6:$B$20,$A22,'S5'!$E$6:$E$20,"Víctor")+COUNTIFS('S5'!$B$6:$B$20,$A22,'S5'!$E$6:$E$20,"Ambos")+COUNTIFS('S6'!$B$6:$B$17,$A22,'S6'!$E$6:$E$17,"Víctor")+COUNTIFS('S6'!$B$6:$B$17,$A22,'S6'!$E$6:$E$17,"Ambos")+COUNTIFS('S7'!$B$6:$B$19,$A22,'S7'!$E$6:$E$19,"Víctor")+COUNTIFS('S7'!$B$6:$B$19,$A22,'S7'!$E$6:$E$19,"Ambos")+COUNTIFS('S8'!$B$6:$B$23,$A22,'S8'!$E$6:$E$23,"Víctor")+COUNTIFS('S8'!$B$6:$B$23,$A22,'S8'!$E$6:$E$23,"Ambos")+COUNTIFS('S9'!$B$6:$B$15,$A22,'S9'!$E$6:$E$15,"Víctor")+COUNTIFS('S9'!$B$6:$B$15,$A22,'S9'!$E$6:$E$15,"Ambos")+COUNTIFS('S10'!$B$6:$B$13,$A22,'S10'!$E$6:$E$13,"Víctor")+COUNTIFS('S10'!$B$6:$B$13,$A22,'S10'!$E$6:$E$13,"Ambos")+COUNTIFS('Holgura'!$B$6:$B$11,$A22,'Holgura'!$E$6:$E$11,"Víctor")+COUNTIFS('Holgura'!$B$6:$B$11,$A22,'Holgura'!$E$6:$E$11,"Ambos")+COUNTIFS('Entrega'!$B$6:$B$9,$A22,'Entrega'!$E$6:$E$9,"Víctor")+COUNTIFS('Entrega'!$B$6:$B$9,$A22,'Entrega'!$E$6:$E$9,"Ambos")+COUNTIFS('Defensa'!$B$6:$B$10,$A22,'Defensa'!$E$6:$E$10,"Víctor")+COUNTIFS('Defensa'!$B$6:$B$10,$A22,'Defensa'!$E$6:$E$10,"Ambos")</f>
         <v/>
       </c>
       <c r="G22" s="21">
-        <f>COUNTIFS('S1'!$B$6:$B$32,$A22,'S1'!$E$6:$E$32,"Diego")+COUNTIFS('S1'!$B$6:$B$32,$A22,'S1'!$E$6:$E$32,"Ambos")+COUNTIFS('S2'!$B$6:$B$23,$A22,'S2'!$E$6:$E$23,"Diego")+COUNTIFS('S2'!$B$6:$B$23,$A22,'S2'!$E$6:$E$23,"Ambos")+COUNTIFS('S3'!$B$6:$B$19,$A22,'S3'!$E$6:$E$19,"Diego")+COUNTIFS('S3'!$B$6:$B$19,$A22,'S3'!$E$6:$E$19,"Ambos")+COUNTIFS('S4'!$B$6:$B$20,$A22,'S4'!$E$6:$E$20,"Diego")+COUNTIFS('S4'!$B$6:$B$20,$A22,'S4'!$E$6:$E$20,"Ambos")+COUNTIFS('S5'!$B$6:$B$20,$A22,'S5'!$E$6:$E$20,"Diego")+COUNTIFS('S5'!$B$6:$B$20,$A22,'S5'!$E$6:$E$20,"Ambos")+COUNTIFS('S6'!$B$6:$B$17,$A22,'S6'!$E$6:$E$17,"Diego")+COUNTIFS('S6'!$B$6:$B$17,$A22,'S6'!$E$6:$E$17,"Ambos")+COUNTIFS('S7'!$B$6:$B$19,$A22,'S7'!$E$6:$E$19,"Diego")+COUNTIFS('S7'!$B$6:$B$19,$A22,'S7'!$E$6:$E$19,"Ambos")+COUNTIFS('S8'!$B$6:$B$23,$A22,'S8'!$E$6:$E$23,"Diego")+COUNTIFS('S8'!$B$6:$B$23,$A22,'S8'!$E$6:$E$23,"Ambos")+COUNTIFS('S9'!$B$6:$B$15,$A22,'S9'!$E$6:$E$15,"Diego")+COUNTIFS('S9'!$B$6:$B$15,$A22,'S9'!$E$6:$E$15,"Ambos")+COUNTIFS('S10'!$B$6:$B$13,$A22,'S10'!$E$6:$E$13,"Diego")+COUNTIFS('S10'!$B$6:$B$13,$A22,'S10'!$E$6:$E$13,"Ambos")+COUNTIFS('Holgura'!$B$6:$B$11,$A22,'Holgura'!$E$6:$E$11,"Diego")+COUNTIFS('Holgura'!$B$6:$B$11,$A22,'Holgura'!$E$6:$E$11,"Ambos")+COUNTIFS('Entrega'!$B$6:$B$9,$A22,'Entrega'!$E$6:$E$9,"Diego")+COUNTIFS('Entrega'!$B$6:$B$9,$A22,'Entrega'!$E$6:$E$9,"Ambos")+COUNTIFS('Defensa'!$B$6:$B$10,$A22,'Defensa'!$E$6:$E$10,"Diego")+COUNTIFS('Defensa'!$B$6:$B$10,$A22,'Defensa'!$E$6:$E$10,"Ambos")</f>
+        <f>COUNTIFS('S1'!$B$6:$B$32,$A22,'S1'!$E$6:$E$32,"Diego")+COUNTIFS('S1'!$B$6:$B$32,$A22,'S1'!$E$6:$E$32,"Ambos")+COUNTIFS('S2'!$B$6:$B$23,$A22,'S2'!$E$6:$E$23,"Diego")+COUNTIFS('S2'!$B$6:$B$23,$A22,'S2'!$E$6:$E$23,"Ambos")+COUNTIFS('S3'!$B$6:$B$24,$A22,'S3'!$E$6:$E$24,"Diego")+COUNTIFS('S3'!$B$6:$B$24,$A22,'S3'!$E$6:$E$24,"Ambos")+COUNTIFS('S4'!$B$6:$B$22,$A22,'S4'!$E$6:$E$22,"Diego")+COUNTIFS('S4'!$B$6:$B$22,$A22,'S4'!$E$6:$E$22,"Ambos")+COUNTIFS('S5'!$B$6:$B$20,$A22,'S5'!$E$6:$E$20,"Diego")+COUNTIFS('S5'!$B$6:$B$20,$A22,'S5'!$E$6:$E$20,"Ambos")+COUNTIFS('S6'!$B$6:$B$17,$A22,'S6'!$E$6:$E$17,"Diego")+COUNTIFS('S6'!$B$6:$B$17,$A22,'S6'!$E$6:$E$17,"Ambos")+COUNTIFS('S7'!$B$6:$B$19,$A22,'S7'!$E$6:$E$19,"Diego")+COUNTIFS('S7'!$B$6:$B$19,$A22,'S7'!$E$6:$E$19,"Ambos")+COUNTIFS('S8'!$B$6:$B$23,$A22,'S8'!$E$6:$E$23,"Diego")+COUNTIFS('S8'!$B$6:$B$23,$A22,'S8'!$E$6:$E$23,"Ambos")+COUNTIFS('S9'!$B$6:$B$15,$A22,'S9'!$E$6:$E$15,"Diego")+COUNTIFS('S9'!$B$6:$B$15,$A22,'S9'!$E$6:$E$15,"Ambos")+COUNTIFS('S10'!$B$6:$B$13,$A22,'S10'!$E$6:$E$13,"Diego")+COUNTIFS('S10'!$B$6:$B$13,$A22,'S10'!$E$6:$E$13,"Ambos")+COUNTIFS('Holgura'!$B$6:$B$11,$A22,'Holgura'!$E$6:$E$11,"Diego")+COUNTIFS('Holgura'!$B$6:$B$11,$A22,'Holgura'!$E$6:$E$11,"Ambos")+COUNTIFS('Entrega'!$B$6:$B$9,$A22,'Entrega'!$E$6:$E$9,"Diego")+COUNTIFS('Entrega'!$B$6:$B$9,$A22,'Entrega'!$E$6:$E$9,"Ambos")+COUNTIFS('Defensa'!$B$6:$B$10,$A22,'Defensa'!$E$6:$E$10,"Diego")+COUNTIFS('Defensa'!$B$6:$B$10,$A22,'Defensa'!$E$6:$E$10,"Ambos")</f>
         <v/>
       </c>
     </row>
@@ -9202,19 +9223,19 @@
         <v/>
       </c>
       <c r="D23" s="21">
-        <f>SUMIFS('S1'!$I$6:$I$32,'S1'!$B$6:$B$32,$A23,'S1'!$E$6:$E$32,"Víctor")+SUMIFS('S1'!$I$6:$I$32,'S1'!$B$6:$B$32,$A23,'S1'!$E$6:$E$32,"Ambos")+SUMIFS('S2'!$I$6:$I$23,'S2'!$B$6:$B$23,$A23,'S2'!$E$6:$E$23,"Víctor")+SUMIFS('S2'!$I$6:$I$23,'S2'!$B$6:$B$23,$A23,'S2'!$E$6:$E$23,"Ambos")+SUMIFS('S3'!$I$6:$I$19,'S3'!$B$6:$B$19,$A23,'S3'!$E$6:$E$19,"Víctor")+SUMIFS('S3'!$I$6:$I$19,'S3'!$B$6:$B$19,$A23,'S3'!$E$6:$E$19,"Ambos")+SUMIFS('S4'!$I$6:$I$20,'S4'!$B$6:$B$20,$A23,'S4'!$E$6:$E$20,"Víctor")+SUMIFS('S4'!$I$6:$I$20,'S4'!$B$6:$B$20,$A23,'S4'!$E$6:$E$20,"Ambos")+SUMIFS('S5'!$I$6:$I$20,'S5'!$B$6:$B$20,$A23,'S5'!$E$6:$E$20,"Víctor")+SUMIFS('S5'!$I$6:$I$20,'S5'!$B$6:$B$20,$A23,'S5'!$E$6:$E$20,"Ambos")+SUMIFS('S6'!$I$6:$I$17,'S6'!$B$6:$B$17,$A23,'S6'!$E$6:$E$17,"Víctor")+SUMIFS('S6'!$I$6:$I$17,'S6'!$B$6:$B$17,$A23,'S6'!$E$6:$E$17,"Ambos")+SUMIFS('S7'!$I$6:$I$19,'S7'!$B$6:$B$19,$A23,'S7'!$E$6:$E$19,"Víctor")+SUMIFS('S7'!$I$6:$I$19,'S7'!$B$6:$B$19,$A23,'S7'!$E$6:$E$19,"Ambos")+SUMIFS('S8'!$I$6:$I$23,'S8'!$B$6:$B$23,$A23,'S8'!$E$6:$E$23,"Víctor")+SUMIFS('S8'!$I$6:$I$23,'S8'!$B$6:$B$23,$A23,'S8'!$E$6:$E$23,"Ambos")+SUMIFS('S9'!$I$6:$I$15,'S9'!$B$6:$B$15,$A23,'S9'!$E$6:$E$15,"Víctor")+SUMIFS('S9'!$I$6:$I$15,'S9'!$B$6:$B$15,$A23,'S9'!$E$6:$E$15,"Ambos")+SUMIFS('S10'!$I$6:$I$13,'S10'!$B$6:$B$13,$A23,'S10'!$E$6:$E$13,"Víctor")+SUMIFS('S10'!$I$6:$I$13,'S10'!$B$6:$B$13,$A23,'S10'!$E$6:$E$13,"Ambos")+SUMIFS('Holgura'!$I$6:$I$11,'Holgura'!$B$6:$B$11,$A23,'Holgura'!$E$6:$E$11,"Víctor")+SUMIFS('Holgura'!$I$6:$I$11,'Holgura'!$B$6:$B$11,$A23,'Holgura'!$E$6:$E$11,"Ambos")+SUMIFS('Entrega'!$I$6:$I$9,'Entrega'!$B$6:$B$9,$A23,'Entrega'!$E$6:$E$9,"Víctor")+SUMIFS('Entrega'!$I$6:$I$9,'Entrega'!$B$6:$B$9,$A23,'Entrega'!$E$6:$E$9,"Ambos")+SUMIFS('Defensa'!$I$6:$I$10,'Defensa'!$B$6:$B$10,$A23,'Defensa'!$E$6:$E$10,"Víctor")+SUMIFS('Defensa'!$I$6:$I$10,'Defensa'!$B$6:$B$10,$A23,'Defensa'!$E$6:$E$10,"Ambos")</f>
+        <f>SUMIFS('S1'!$I$6:$I$32,'S1'!$B$6:$B$32,$A23,'S1'!$E$6:$E$32,"Víctor")+SUMIFS('S1'!$I$6:$I$32,'S1'!$B$6:$B$32,$A23,'S1'!$E$6:$E$32,"Ambos")+SUMIFS('S2'!$I$6:$I$23,'S2'!$B$6:$B$23,$A23,'S2'!$E$6:$E$23,"Víctor")+SUMIFS('S2'!$I$6:$I$23,'S2'!$B$6:$B$23,$A23,'S2'!$E$6:$E$23,"Ambos")+SUMIFS('S3'!$I$6:$I$24,'S3'!$B$6:$B$24,$A23,'S3'!$E$6:$E$24,"Víctor")+SUMIFS('S3'!$I$6:$I$24,'S3'!$B$6:$B$24,$A23,'S3'!$E$6:$E$24,"Ambos")+SUMIFS('S4'!$I$6:$I$22,'S4'!$B$6:$B$22,$A23,'S4'!$E$6:$E$22,"Víctor")+SUMIFS('S4'!$I$6:$I$22,'S4'!$B$6:$B$22,$A23,'S4'!$E$6:$E$22,"Ambos")+SUMIFS('S5'!$I$6:$I$20,'S5'!$B$6:$B$20,$A23,'S5'!$E$6:$E$20,"Víctor")+SUMIFS('S5'!$I$6:$I$20,'S5'!$B$6:$B$20,$A23,'S5'!$E$6:$E$20,"Ambos")+SUMIFS('S6'!$I$6:$I$17,'S6'!$B$6:$B$17,$A23,'S6'!$E$6:$E$17,"Víctor")+SUMIFS('S6'!$I$6:$I$17,'S6'!$B$6:$B$17,$A23,'S6'!$E$6:$E$17,"Ambos")+SUMIFS('S7'!$I$6:$I$19,'S7'!$B$6:$B$19,$A23,'S7'!$E$6:$E$19,"Víctor")+SUMIFS('S7'!$I$6:$I$19,'S7'!$B$6:$B$19,$A23,'S7'!$E$6:$E$19,"Ambos")+SUMIFS('S8'!$I$6:$I$23,'S8'!$B$6:$B$23,$A23,'S8'!$E$6:$E$23,"Víctor")+SUMIFS('S8'!$I$6:$I$23,'S8'!$B$6:$B$23,$A23,'S8'!$E$6:$E$23,"Ambos")+SUMIFS('S9'!$I$6:$I$15,'S9'!$B$6:$B$15,$A23,'S9'!$E$6:$E$15,"Víctor")+SUMIFS('S9'!$I$6:$I$15,'S9'!$B$6:$B$15,$A23,'S9'!$E$6:$E$15,"Ambos")+SUMIFS('S10'!$I$6:$I$13,'S10'!$B$6:$B$13,$A23,'S10'!$E$6:$E$13,"Víctor")+SUMIFS('S10'!$I$6:$I$13,'S10'!$B$6:$B$13,$A23,'S10'!$E$6:$E$13,"Ambos")+SUMIFS('Holgura'!$I$6:$I$11,'Holgura'!$B$6:$B$11,$A23,'Holgura'!$E$6:$E$11,"Víctor")+SUMIFS('Holgura'!$I$6:$I$11,'Holgura'!$B$6:$B$11,$A23,'Holgura'!$E$6:$E$11,"Ambos")+SUMIFS('Entrega'!$I$6:$I$9,'Entrega'!$B$6:$B$9,$A23,'Entrega'!$E$6:$E$9,"Víctor")+SUMIFS('Entrega'!$I$6:$I$9,'Entrega'!$B$6:$B$9,$A23,'Entrega'!$E$6:$E$9,"Ambos")+SUMIFS('Defensa'!$I$6:$I$10,'Defensa'!$B$6:$B$10,$A23,'Defensa'!$E$6:$E$10,"Víctor")+SUMIFS('Defensa'!$I$6:$I$10,'Defensa'!$B$6:$B$10,$A23,'Defensa'!$E$6:$E$10,"Ambos")</f>
         <v/>
       </c>
       <c r="E23" s="21">
-        <f>SUMIFS('S1'!$I$6:$I$32,'S1'!$B$6:$B$32,$A23,'S1'!$E$6:$E$32,"Diego")+SUMIFS('S1'!$I$6:$I$32,'S1'!$B$6:$B$32,$A23,'S1'!$E$6:$E$32,"Ambos")+SUMIFS('S2'!$I$6:$I$23,'S2'!$B$6:$B$23,$A23,'S2'!$E$6:$E$23,"Diego")+SUMIFS('S2'!$I$6:$I$23,'S2'!$B$6:$B$23,$A23,'S2'!$E$6:$E$23,"Ambos")+SUMIFS('S3'!$I$6:$I$19,'S3'!$B$6:$B$19,$A23,'S3'!$E$6:$E$19,"Diego")+SUMIFS('S3'!$I$6:$I$19,'S3'!$B$6:$B$19,$A23,'S3'!$E$6:$E$19,"Ambos")+SUMIFS('S4'!$I$6:$I$20,'S4'!$B$6:$B$20,$A23,'S4'!$E$6:$E$20,"Diego")+SUMIFS('S4'!$I$6:$I$20,'S4'!$B$6:$B$20,$A23,'S4'!$E$6:$E$20,"Ambos")+SUMIFS('S5'!$I$6:$I$20,'S5'!$B$6:$B$20,$A23,'S5'!$E$6:$E$20,"Diego")+SUMIFS('S5'!$I$6:$I$20,'S5'!$B$6:$B$20,$A23,'S5'!$E$6:$E$20,"Ambos")+SUMIFS('S6'!$I$6:$I$17,'S6'!$B$6:$B$17,$A23,'S6'!$E$6:$E$17,"Diego")+SUMIFS('S6'!$I$6:$I$17,'S6'!$B$6:$B$17,$A23,'S6'!$E$6:$E$17,"Ambos")+SUMIFS('S7'!$I$6:$I$19,'S7'!$B$6:$B$19,$A23,'S7'!$E$6:$E$19,"Diego")+SUMIFS('S7'!$I$6:$I$19,'S7'!$B$6:$B$19,$A23,'S7'!$E$6:$E$19,"Ambos")+SUMIFS('S8'!$I$6:$I$23,'S8'!$B$6:$B$23,$A23,'S8'!$E$6:$E$23,"Diego")+SUMIFS('S8'!$I$6:$I$23,'S8'!$B$6:$B$23,$A23,'S8'!$E$6:$E$23,"Ambos")+SUMIFS('S9'!$I$6:$I$15,'S9'!$B$6:$B$15,$A23,'S9'!$E$6:$E$15,"Diego")+SUMIFS('S9'!$I$6:$I$15,'S9'!$B$6:$B$15,$A23,'S9'!$E$6:$E$15,"Ambos")+SUMIFS('S10'!$I$6:$I$13,'S10'!$B$6:$B$13,$A23,'S10'!$E$6:$E$13,"Diego")+SUMIFS('S10'!$I$6:$I$13,'S10'!$B$6:$B$13,$A23,'S10'!$E$6:$E$13,"Ambos")+SUMIFS('Holgura'!$I$6:$I$11,'Holgura'!$B$6:$B$11,$A23,'Holgura'!$E$6:$E$11,"Diego")+SUMIFS('Holgura'!$I$6:$I$11,'Holgura'!$B$6:$B$11,$A23,'Holgura'!$E$6:$E$11,"Ambos")+SUMIFS('Entrega'!$I$6:$I$9,'Entrega'!$B$6:$B$9,$A23,'Entrega'!$E$6:$E$9,"Diego")+SUMIFS('Entrega'!$I$6:$I$9,'Entrega'!$B$6:$B$9,$A23,'Entrega'!$E$6:$E$9,"Ambos")+SUMIFS('Defensa'!$I$6:$I$10,'Defensa'!$B$6:$B$10,$A23,'Defensa'!$E$6:$E$10,"Diego")+SUMIFS('Defensa'!$I$6:$I$10,'Defensa'!$B$6:$B$10,$A23,'Defensa'!$E$6:$E$10,"Ambos")</f>
+        <f>SUMIFS('S1'!$I$6:$I$32,'S1'!$B$6:$B$32,$A23,'S1'!$E$6:$E$32,"Diego")+SUMIFS('S1'!$I$6:$I$32,'S1'!$B$6:$B$32,$A23,'S1'!$E$6:$E$32,"Ambos")+SUMIFS('S2'!$I$6:$I$23,'S2'!$B$6:$B$23,$A23,'S2'!$E$6:$E$23,"Diego")+SUMIFS('S2'!$I$6:$I$23,'S2'!$B$6:$B$23,$A23,'S2'!$E$6:$E$23,"Ambos")+SUMIFS('S3'!$I$6:$I$24,'S3'!$B$6:$B$24,$A23,'S3'!$E$6:$E$24,"Diego")+SUMIFS('S3'!$I$6:$I$24,'S3'!$B$6:$B$24,$A23,'S3'!$E$6:$E$24,"Ambos")+SUMIFS('S4'!$I$6:$I$22,'S4'!$B$6:$B$22,$A23,'S4'!$E$6:$E$22,"Diego")+SUMIFS('S4'!$I$6:$I$22,'S4'!$B$6:$B$22,$A23,'S4'!$E$6:$E$22,"Ambos")+SUMIFS('S5'!$I$6:$I$20,'S5'!$B$6:$B$20,$A23,'S5'!$E$6:$E$20,"Diego")+SUMIFS('S5'!$I$6:$I$20,'S5'!$B$6:$B$20,$A23,'S5'!$E$6:$E$20,"Ambos")+SUMIFS('S6'!$I$6:$I$17,'S6'!$B$6:$B$17,$A23,'S6'!$E$6:$E$17,"Diego")+SUMIFS('S6'!$I$6:$I$17,'S6'!$B$6:$B$17,$A23,'S6'!$E$6:$E$17,"Ambos")+SUMIFS('S7'!$I$6:$I$19,'S7'!$B$6:$B$19,$A23,'S7'!$E$6:$E$19,"Diego")+SUMIFS('S7'!$I$6:$I$19,'S7'!$B$6:$B$19,$A23,'S7'!$E$6:$E$19,"Ambos")+SUMIFS('S8'!$I$6:$I$23,'S8'!$B$6:$B$23,$A23,'S8'!$E$6:$E$23,"Diego")+SUMIFS('S8'!$I$6:$I$23,'S8'!$B$6:$B$23,$A23,'S8'!$E$6:$E$23,"Ambos")+SUMIFS('S9'!$I$6:$I$15,'S9'!$B$6:$B$15,$A23,'S9'!$E$6:$E$15,"Diego")+SUMIFS('S9'!$I$6:$I$15,'S9'!$B$6:$B$15,$A23,'S9'!$E$6:$E$15,"Ambos")+SUMIFS('S10'!$I$6:$I$13,'S10'!$B$6:$B$13,$A23,'S10'!$E$6:$E$13,"Diego")+SUMIFS('S10'!$I$6:$I$13,'S10'!$B$6:$B$13,$A23,'S10'!$E$6:$E$13,"Ambos")+SUMIFS('Holgura'!$I$6:$I$11,'Holgura'!$B$6:$B$11,$A23,'Holgura'!$E$6:$E$11,"Diego")+SUMIFS('Holgura'!$I$6:$I$11,'Holgura'!$B$6:$B$11,$A23,'Holgura'!$E$6:$E$11,"Ambos")+SUMIFS('Entrega'!$I$6:$I$9,'Entrega'!$B$6:$B$9,$A23,'Entrega'!$E$6:$E$9,"Diego")+SUMIFS('Entrega'!$I$6:$I$9,'Entrega'!$B$6:$B$9,$A23,'Entrega'!$E$6:$E$9,"Ambos")+SUMIFS('Defensa'!$I$6:$I$10,'Defensa'!$B$6:$B$10,$A23,'Defensa'!$E$6:$E$10,"Diego")+SUMIFS('Defensa'!$I$6:$I$10,'Defensa'!$B$6:$B$10,$A23,'Defensa'!$E$6:$E$10,"Ambos")</f>
         <v/>
       </c>
       <c r="F23" s="21">
-        <f>COUNTIFS('S1'!$B$6:$B$32,$A23,'S1'!$E$6:$E$32,"Víctor")+COUNTIFS('S1'!$B$6:$B$32,$A23,'S1'!$E$6:$E$32,"Ambos")+COUNTIFS('S2'!$B$6:$B$23,$A23,'S2'!$E$6:$E$23,"Víctor")+COUNTIFS('S2'!$B$6:$B$23,$A23,'S2'!$E$6:$E$23,"Ambos")+COUNTIFS('S3'!$B$6:$B$19,$A23,'S3'!$E$6:$E$19,"Víctor")+COUNTIFS('S3'!$B$6:$B$19,$A23,'S3'!$E$6:$E$19,"Ambos")+COUNTIFS('S4'!$B$6:$B$20,$A23,'S4'!$E$6:$E$20,"Víctor")+COUNTIFS('S4'!$B$6:$B$20,$A23,'S4'!$E$6:$E$20,"Ambos")+COUNTIFS('S5'!$B$6:$B$20,$A23,'S5'!$E$6:$E$20,"Víctor")+COUNTIFS('S5'!$B$6:$B$20,$A23,'S5'!$E$6:$E$20,"Ambos")+COUNTIFS('S6'!$B$6:$B$17,$A23,'S6'!$E$6:$E$17,"Víctor")+COUNTIFS('S6'!$B$6:$B$17,$A23,'S6'!$E$6:$E$17,"Ambos")+COUNTIFS('S7'!$B$6:$B$19,$A23,'S7'!$E$6:$E$19,"Víctor")+COUNTIFS('S7'!$B$6:$B$19,$A23,'S7'!$E$6:$E$19,"Ambos")+COUNTIFS('S8'!$B$6:$B$23,$A23,'S8'!$E$6:$E$23,"Víctor")+COUNTIFS('S8'!$B$6:$B$23,$A23,'S8'!$E$6:$E$23,"Ambos")+COUNTIFS('S9'!$B$6:$B$15,$A23,'S9'!$E$6:$E$15,"Víctor")+COUNTIFS('S9'!$B$6:$B$15,$A23,'S9'!$E$6:$E$15,"Ambos")+COUNTIFS('S10'!$B$6:$B$13,$A23,'S10'!$E$6:$E$13,"Víctor")+COUNTIFS('S10'!$B$6:$B$13,$A23,'S10'!$E$6:$E$13,"Ambos")+COUNTIFS('Holgura'!$B$6:$B$11,$A23,'Holgura'!$E$6:$E$11,"Víctor")+COUNTIFS('Holgura'!$B$6:$B$11,$A23,'Holgura'!$E$6:$E$11,"Ambos")+COUNTIFS('Entrega'!$B$6:$B$9,$A23,'Entrega'!$E$6:$E$9,"Víctor")+COUNTIFS('Entrega'!$B$6:$B$9,$A23,'Entrega'!$E$6:$E$9,"Ambos")+COUNTIFS('Defensa'!$B$6:$B$10,$A23,'Defensa'!$E$6:$E$10,"Víctor")+COUNTIFS('Defensa'!$B$6:$B$10,$A23,'Defensa'!$E$6:$E$10,"Ambos")</f>
+        <f>COUNTIFS('S1'!$B$6:$B$32,$A23,'S1'!$E$6:$E$32,"Víctor")+COUNTIFS('S1'!$B$6:$B$32,$A23,'S1'!$E$6:$E$32,"Ambos")+COUNTIFS('S2'!$B$6:$B$23,$A23,'S2'!$E$6:$E$23,"Víctor")+COUNTIFS('S2'!$B$6:$B$23,$A23,'S2'!$E$6:$E$23,"Ambos")+COUNTIFS('S3'!$B$6:$B$24,$A23,'S3'!$E$6:$E$24,"Víctor")+COUNTIFS('S3'!$B$6:$B$24,$A23,'S3'!$E$6:$E$24,"Ambos")+COUNTIFS('S4'!$B$6:$B$22,$A23,'S4'!$E$6:$E$22,"Víctor")+COUNTIFS('S4'!$B$6:$B$22,$A23,'S4'!$E$6:$E$22,"Ambos")+COUNTIFS('S5'!$B$6:$B$20,$A23,'S5'!$E$6:$E$20,"Víctor")+COUNTIFS('S5'!$B$6:$B$20,$A23,'S5'!$E$6:$E$20,"Ambos")+COUNTIFS('S6'!$B$6:$B$17,$A23,'S6'!$E$6:$E$17,"Víctor")+COUNTIFS('S6'!$B$6:$B$17,$A23,'S6'!$E$6:$E$17,"Ambos")+COUNTIFS('S7'!$B$6:$B$19,$A23,'S7'!$E$6:$E$19,"Víctor")+COUNTIFS('S7'!$B$6:$B$19,$A23,'S7'!$E$6:$E$19,"Ambos")+COUNTIFS('S8'!$B$6:$B$23,$A23,'S8'!$E$6:$E$23,"Víctor")+COUNTIFS('S8'!$B$6:$B$23,$A23,'S8'!$E$6:$E$23,"Ambos")+COUNTIFS('S9'!$B$6:$B$15,$A23,'S9'!$E$6:$E$15,"Víctor")+COUNTIFS('S9'!$B$6:$B$15,$A23,'S9'!$E$6:$E$15,"Ambos")+COUNTIFS('S10'!$B$6:$B$13,$A23,'S10'!$E$6:$E$13,"Víctor")+COUNTIFS('S10'!$B$6:$B$13,$A23,'S10'!$E$6:$E$13,"Ambos")+COUNTIFS('Holgura'!$B$6:$B$11,$A23,'Holgura'!$E$6:$E$11,"Víctor")+COUNTIFS('Holgura'!$B$6:$B$11,$A23,'Holgura'!$E$6:$E$11,"Ambos")+COUNTIFS('Entrega'!$B$6:$B$9,$A23,'Entrega'!$E$6:$E$9,"Víctor")+COUNTIFS('Entrega'!$B$6:$B$9,$A23,'Entrega'!$E$6:$E$9,"Ambos")+COUNTIFS('Defensa'!$B$6:$B$10,$A23,'Defensa'!$E$6:$E$10,"Víctor")+COUNTIFS('Defensa'!$B$6:$B$10,$A23,'Defensa'!$E$6:$E$10,"Ambos")</f>
         <v/>
       </c>
       <c r="G23" s="21">
-        <f>COUNTIFS('S1'!$B$6:$B$32,$A23,'S1'!$E$6:$E$32,"Diego")+COUNTIFS('S1'!$B$6:$B$32,$A23,'S1'!$E$6:$E$32,"Ambos")+COUNTIFS('S2'!$B$6:$B$23,$A23,'S2'!$E$6:$E$23,"Diego")+COUNTIFS('S2'!$B$6:$B$23,$A23,'S2'!$E$6:$E$23,"Ambos")+COUNTIFS('S3'!$B$6:$B$19,$A23,'S3'!$E$6:$E$19,"Diego")+COUNTIFS('S3'!$B$6:$B$19,$A23,'S3'!$E$6:$E$19,"Ambos")+COUNTIFS('S4'!$B$6:$B$20,$A23,'S4'!$E$6:$E$20,"Diego")+COUNTIFS('S4'!$B$6:$B$20,$A23,'S4'!$E$6:$E$20,"Ambos")+COUNTIFS('S5'!$B$6:$B$20,$A23,'S5'!$E$6:$E$20,"Diego")+COUNTIFS('S5'!$B$6:$B$20,$A23,'S5'!$E$6:$E$20,"Ambos")+COUNTIFS('S6'!$B$6:$B$17,$A23,'S6'!$E$6:$E$17,"Diego")+COUNTIFS('S6'!$B$6:$B$17,$A23,'S6'!$E$6:$E$17,"Ambos")+COUNTIFS('S7'!$B$6:$B$19,$A23,'S7'!$E$6:$E$19,"Diego")+COUNTIFS('S7'!$B$6:$B$19,$A23,'S7'!$E$6:$E$19,"Ambos")+COUNTIFS('S8'!$B$6:$B$23,$A23,'S8'!$E$6:$E$23,"Diego")+COUNTIFS('S8'!$B$6:$B$23,$A23,'S8'!$E$6:$E$23,"Ambos")+COUNTIFS('S9'!$B$6:$B$15,$A23,'S9'!$E$6:$E$15,"Diego")+COUNTIFS('S9'!$B$6:$B$15,$A23,'S9'!$E$6:$E$15,"Ambos")+COUNTIFS('S10'!$B$6:$B$13,$A23,'S10'!$E$6:$E$13,"Diego")+COUNTIFS('S10'!$B$6:$B$13,$A23,'S10'!$E$6:$E$13,"Ambos")+COUNTIFS('Holgura'!$B$6:$B$11,$A23,'Holgura'!$E$6:$E$11,"Diego")+COUNTIFS('Holgura'!$B$6:$B$11,$A23,'Holgura'!$E$6:$E$11,"Ambos")+COUNTIFS('Entrega'!$B$6:$B$9,$A23,'Entrega'!$E$6:$E$9,"Diego")+COUNTIFS('Entrega'!$B$6:$B$9,$A23,'Entrega'!$E$6:$E$9,"Ambos")+COUNTIFS('Defensa'!$B$6:$B$10,$A23,'Defensa'!$E$6:$E$10,"Diego")+COUNTIFS('Defensa'!$B$6:$B$10,$A23,'Defensa'!$E$6:$E$10,"Ambos")</f>
+        <f>COUNTIFS('S1'!$B$6:$B$32,$A23,'S1'!$E$6:$E$32,"Diego")+COUNTIFS('S1'!$B$6:$B$32,$A23,'S1'!$E$6:$E$32,"Ambos")+COUNTIFS('S2'!$B$6:$B$23,$A23,'S2'!$E$6:$E$23,"Diego")+COUNTIFS('S2'!$B$6:$B$23,$A23,'S2'!$E$6:$E$23,"Ambos")+COUNTIFS('S3'!$B$6:$B$24,$A23,'S3'!$E$6:$E$24,"Diego")+COUNTIFS('S3'!$B$6:$B$24,$A23,'S3'!$E$6:$E$24,"Ambos")+COUNTIFS('S4'!$B$6:$B$22,$A23,'S4'!$E$6:$E$22,"Diego")+COUNTIFS('S4'!$B$6:$B$22,$A23,'S4'!$E$6:$E$22,"Ambos")+COUNTIFS('S5'!$B$6:$B$20,$A23,'S5'!$E$6:$E$20,"Diego")+COUNTIFS('S5'!$B$6:$B$20,$A23,'S5'!$E$6:$E$20,"Ambos")+COUNTIFS('S6'!$B$6:$B$17,$A23,'S6'!$E$6:$E$17,"Diego")+COUNTIFS('S6'!$B$6:$B$17,$A23,'S6'!$E$6:$E$17,"Ambos")+COUNTIFS('S7'!$B$6:$B$19,$A23,'S7'!$E$6:$E$19,"Diego")+COUNTIFS('S7'!$B$6:$B$19,$A23,'S7'!$E$6:$E$19,"Ambos")+COUNTIFS('S8'!$B$6:$B$23,$A23,'S8'!$E$6:$E$23,"Diego")+COUNTIFS('S8'!$B$6:$B$23,$A23,'S8'!$E$6:$E$23,"Ambos")+COUNTIFS('S9'!$B$6:$B$15,$A23,'S9'!$E$6:$E$15,"Diego")+COUNTIFS('S9'!$B$6:$B$15,$A23,'S9'!$E$6:$E$15,"Ambos")+COUNTIFS('S10'!$B$6:$B$13,$A23,'S10'!$E$6:$E$13,"Diego")+COUNTIFS('S10'!$B$6:$B$13,$A23,'S10'!$E$6:$E$13,"Ambos")+COUNTIFS('Holgura'!$B$6:$B$11,$A23,'Holgura'!$E$6:$E$11,"Diego")+COUNTIFS('Holgura'!$B$6:$B$11,$A23,'Holgura'!$E$6:$E$11,"Ambos")+COUNTIFS('Entrega'!$B$6:$B$9,$A23,'Entrega'!$E$6:$E$9,"Diego")+COUNTIFS('Entrega'!$B$6:$B$9,$A23,'Entrega'!$E$6:$E$9,"Ambos")+COUNTIFS('Defensa'!$B$6:$B$10,$A23,'Defensa'!$E$6:$E$10,"Diego")+COUNTIFS('Defensa'!$B$6:$B$10,$A23,'Defensa'!$E$6:$E$10,"Ambos")</f>
         <v/>
       </c>
     </row>
@@ -9231,19 +9252,19 @@
         <v/>
       </c>
       <c r="D24" s="21">
-        <f>SUMIFS('S1'!$I$6:$I$32,'S1'!$B$6:$B$32,$A24,'S1'!$E$6:$E$32,"Víctor")+SUMIFS('S1'!$I$6:$I$32,'S1'!$B$6:$B$32,$A24,'S1'!$E$6:$E$32,"Ambos")+SUMIFS('S2'!$I$6:$I$23,'S2'!$B$6:$B$23,$A24,'S2'!$E$6:$E$23,"Víctor")+SUMIFS('S2'!$I$6:$I$23,'S2'!$B$6:$B$23,$A24,'S2'!$E$6:$E$23,"Ambos")+SUMIFS('S3'!$I$6:$I$19,'S3'!$B$6:$B$19,$A24,'S3'!$E$6:$E$19,"Víctor")+SUMIFS('S3'!$I$6:$I$19,'S3'!$B$6:$B$19,$A24,'S3'!$E$6:$E$19,"Ambos")+SUMIFS('S4'!$I$6:$I$20,'S4'!$B$6:$B$20,$A24,'S4'!$E$6:$E$20,"Víctor")+SUMIFS('S4'!$I$6:$I$20,'S4'!$B$6:$B$20,$A24,'S4'!$E$6:$E$20,"Ambos")+SUMIFS('S5'!$I$6:$I$20,'S5'!$B$6:$B$20,$A24,'S5'!$E$6:$E$20,"Víctor")+SUMIFS('S5'!$I$6:$I$20,'S5'!$B$6:$B$20,$A24,'S5'!$E$6:$E$20,"Ambos")+SUMIFS('S6'!$I$6:$I$17,'S6'!$B$6:$B$17,$A24,'S6'!$E$6:$E$17,"Víctor")+SUMIFS('S6'!$I$6:$I$17,'S6'!$B$6:$B$17,$A24,'S6'!$E$6:$E$17,"Ambos")+SUMIFS('S7'!$I$6:$I$19,'S7'!$B$6:$B$19,$A24,'S7'!$E$6:$E$19,"Víctor")+SUMIFS('S7'!$I$6:$I$19,'S7'!$B$6:$B$19,$A24,'S7'!$E$6:$E$19,"Ambos")+SUMIFS('S8'!$I$6:$I$23,'S8'!$B$6:$B$23,$A24,'S8'!$E$6:$E$23,"Víctor")+SUMIFS('S8'!$I$6:$I$23,'S8'!$B$6:$B$23,$A24,'S8'!$E$6:$E$23,"Ambos")+SUMIFS('S9'!$I$6:$I$15,'S9'!$B$6:$B$15,$A24,'S9'!$E$6:$E$15,"Víctor")+SUMIFS('S9'!$I$6:$I$15,'S9'!$B$6:$B$15,$A24,'S9'!$E$6:$E$15,"Ambos")+SUMIFS('S10'!$I$6:$I$13,'S10'!$B$6:$B$13,$A24,'S10'!$E$6:$E$13,"Víctor")+SUMIFS('S10'!$I$6:$I$13,'S10'!$B$6:$B$13,$A24,'S10'!$E$6:$E$13,"Ambos")+SUMIFS('Holgura'!$I$6:$I$11,'Holgura'!$B$6:$B$11,$A24,'Holgura'!$E$6:$E$11,"Víctor")+SUMIFS('Holgura'!$I$6:$I$11,'Holgura'!$B$6:$B$11,$A24,'Holgura'!$E$6:$E$11,"Ambos")+SUMIFS('Entrega'!$I$6:$I$9,'Entrega'!$B$6:$B$9,$A24,'Entrega'!$E$6:$E$9,"Víctor")+SUMIFS('Entrega'!$I$6:$I$9,'Entrega'!$B$6:$B$9,$A24,'Entrega'!$E$6:$E$9,"Ambos")+SUMIFS('Defensa'!$I$6:$I$10,'Defensa'!$B$6:$B$10,$A24,'Defensa'!$E$6:$E$10,"Víctor")+SUMIFS('Defensa'!$I$6:$I$10,'Defensa'!$B$6:$B$10,$A24,'Defensa'!$E$6:$E$10,"Ambos")</f>
+        <f>SUMIFS('S1'!$I$6:$I$32,'S1'!$B$6:$B$32,$A24,'S1'!$E$6:$E$32,"Víctor")+SUMIFS('S1'!$I$6:$I$32,'S1'!$B$6:$B$32,$A24,'S1'!$E$6:$E$32,"Ambos")+SUMIFS('S2'!$I$6:$I$23,'S2'!$B$6:$B$23,$A24,'S2'!$E$6:$E$23,"Víctor")+SUMIFS('S2'!$I$6:$I$23,'S2'!$B$6:$B$23,$A24,'S2'!$E$6:$E$23,"Ambos")+SUMIFS('S3'!$I$6:$I$24,'S3'!$B$6:$B$24,$A24,'S3'!$E$6:$E$24,"Víctor")+SUMIFS('S3'!$I$6:$I$24,'S3'!$B$6:$B$24,$A24,'S3'!$E$6:$E$24,"Ambos")+SUMIFS('S4'!$I$6:$I$22,'S4'!$B$6:$B$22,$A24,'S4'!$E$6:$E$22,"Víctor")+SUMIFS('S4'!$I$6:$I$22,'S4'!$B$6:$B$22,$A24,'S4'!$E$6:$E$22,"Ambos")+SUMIFS('S5'!$I$6:$I$20,'S5'!$B$6:$B$20,$A24,'S5'!$E$6:$E$20,"Víctor")+SUMIFS('S5'!$I$6:$I$20,'S5'!$B$6:$B$20,$A24,'S5'!$E$6:$E$20,"Ambos")+SUMIFS('S6'!$I$6:$I$17,'S6'!$B$6:$B$17,$A24,'S6'!$E$6:$E$17,"Víctor")+SUMIFS('S6'!$I$6:$I$17,'S6'!$B$6:$B$17,$A24,'S6'!$E$6:$E$17,"Ambos")+SUMIFS('S7'!$I$6:$I$19,'S7'!$B$6:$B$19,$A24,'S7'!$E$6:$E$19,"Víctor")+SUMIFS('S7'!$I$6:$I$19,'S7'!$B$6:$B$19,$A24,'S7'!$E$6:$E$19,"Ambos")+SUMIFS('S8'!$I$6:$I$23,'S8'!$B$6:$B$23,$A24,'S8'!$E$6:$E$23,"Víctor")+SUMIFS('S8'!$I$6:$I$23,'S8'!$B$6:$B$23,$A24,'S8'!$E$6:$E$23,"Ambos")+SUMIFS('S9'!$I$6:$I$15,'S9'!$B$6:$B$15,$A24,'S9'!$E$6:$E$15,"Víctor")+SUMIFS('S9'!$I$6:$I$15,'S9'!$B$6:$B$15,$A24,'S9'!$E$6:$E$15,"Ambos")+SUMIFS('S10'!$I$6:$I$13,'S10'!$B$6:$B$13,$A24,'S10'!$E$6:$E$13,"Víctor")+SUMIFS('S10'!$I$6:$I$13,'S10'!$B$6:$B$13,$A24,'S10'!$E$6:$E$13,"Ambos")+SUMIFS('Holgura'!$I$6:$I$11,'Holgura'!$B$6:$B$11,$A24,'Holgura'!$E$6:$E$11,"Víctor")+SUMIFS('Holgura'!$I$6:$I$11,'Holgura'!$B$6:$B$11,$A24,'Holgura'!$E$6:$E$11,"Ambos")+SUMIFS('Entrega'!$I$6:$I$9,'Entrega'!$B$6:$B$9,$A24,'Entrega'!$E$6:$E$9,"Víctor")+SUMIFS('Entrega'!$I$6:$I$9,'Entrega'!$B$6:$B$9,$A24,'Entrega'!$E$6:$E$9,"Ambos")+SUMIFS('Defensa'!$I$6:$I$10,'Defensa'!$B$6:$B$10,$A24,'Defensa'!$E$6:$E$10,"Víctor")+SUMIFS('Defensa'!$I$6:$I$10,'Defensa'!$B$6:$B$10,$A24,'Defensa'!$E$6:$E$10,"Ambos")</f>
         <v/>
       </c>
       <c r="E24" s="21">
-        <f>SUMIFS('S1'!$I$6:$I$32,'S1'!$B$6:$B$32,$A24,'S1'!$E$6:$E$32,"Diego")+SUMIFS('S1'!$I$6:$I$32,'S1'!$B$6:$B$32,$A24,'S1'!$E$6:$E$32,"Ambos")+SUMIFS('S2'!$I$6:$I$23,'S2'!$B$6:$B$23,$A24,'S2'!$E$6:$E$23,"Diego")+SUMIFS('S2'!$I$6:$I$23,'S2'!$B$6:$B$23,$A24,'S2'!$E$6:$E$23,"Ambos")+SUMIFS('S3'!$I$6:$I$19,'S3'!$B$6:$B$19,$A24,'S3'!$E$6:$E$19,"Diego")+SUMIFS('S3'!$I$6:$I$19,'S3'!$B$6:$B$19,$A24,'S3'!$E$6:$E$19,"Ambos")+SUMIFS('S4'!$I$6:$I$20,'S4'!$B$6:$B$20,$A24,'S4'!$E$6:$E$20,"Diego")+SUMIFS('S4'!$I$6:$I$20,'S4'!$B$6:$B$20,$A24,'S4'!$E$6:$E$20,"Ambos")+SUMIFS('S5'!$I$6:$I$20,'S5'!$B$6:$B$20,$A24,'S5'!$E$6:$E$20,"Diego")+SUMIFS('S5'!$I$6:$I$20,'S5'!$B$6:$B$20,$A24,'S5'!$E$6:$E$20,"Ambos")+SUMIFS('S6'!$I$6:$I$17,'S6'!$B$6:$B$17,$A24,'S6'!$E$6:$E$17,"Diego")+SUMIFS('S6'!$I$6:$I$17,'S6'!$B$6:$B$17,$A24,'S6'!$E$6:$E$17,"Ambos")+SUMIFS('S7'!$I$6:$I$19,'S7'!$B$6:$B$19,$A24,'S7'!$E$6:$E$19,"Diego")+SUMIFS('S7'!$I$6:$I$19,'S7'!$B$6:$B$19,$A24,'S7'!$E$6:$E$19,"Ambos")+SUMIFS('S8'!$I$6:$I$23,'S8'!$B$6:$B$23,$A24,'S8'!$E$6:$E$23,"Diego")+SUMIFS('S8'!$I$6:$I$23,'S8'!$B$6:$B$23,$A24,'S8'!$E$6:$E$23,"Ambos")+SUMIFS('S9'!$I$6:$I$15,'S9'!$B$6:$B$15,$A24,'S9'!$E$6:$E$15,"Diego")+SUMIFS('S9'!$I$6:$I$15,'S9'!$B$6:$B$15,$A24,'S9'!$E$6:$E$15,"Ambos")+SUMIFS('S10'!$I$6:$I$13,'S10'!$B$6:$B$13,$A24,'S10'!$E$6:$E$13,"Diego")+SUMIFS('S10'!$I$6:$I$13,'S10'!$B$6:$B$13,$A24,'S10'!$E$6:$E$13,"Ambos")+SUMIFS('Holgura'!$I$6:$I$11,'Holgura'!$B$6:$B$11,$A24,'Holgura'!$E$6:$E$11,"Diego")+SUMIFS('Holgura'!$I$6:$I$11,'Holgura'!$B$6:$B$11,$A24,'Holgura'!$E$6:$E$11,"Ambos")+SUMIFS('Entrega'!$I$6:$I$9,'Entrega'!$B$6:$B$9,$A24,'Entrega'!$E$6:$E$9,"Diego")+SUMIFS('Entrega'!$I$6:$I$9,'Entrega'!$B$6:$B$9,$A24,'Entrega'!$E$6:$E$9,"Ambos")+SUMIFS('Defensa'!$I$6:$I$10,'Defensa'!$B$6:$B$10,$A24,'Defensa'!$E$6:$E$10,"Diego")+SUMIFS('Defensa'!$I$6:$I$10,'Defensa'!$B$6:$B$10,$A24,'Defensa'!$E$6:$E$10,"Ambos")</f>
+        <f>SUMIFS('S1'!$I$6:$I$32,'S1'!$B$6:$B$32,$A24,'S1'!$E$6:$E$32,"Diego")+SUMIFS('S1'!$I$6:$I$32,'S1'!$B$6:$B$32,$A24,'S1'!$E$6:$E$32,"Ambos")+SUMIFS('S2'!$I$6:$I$23,'S2'!$B$6:$B$23,$A24,'S2'!$E$6:$E$23,"Diego")+SUMIFS('S2'!$I$6:$I$23,'S2'!$B$6:$B$23,$A24,'S2'!$E$6:$E$23,"Ambos")+SUMIFS('S3'!$I$6:$I$24,'S3'!$B$6:$B$24,$A24,'S3'!$E$6:$E$24,"Diego")+SUMIFS('S3'!$I$6:$I$24,'S3'!$B$6:$B$24,$A24,'S3'!$E$6:$E$24,"Ambos")+SUMIFS('S4'!$I$6:$I$22,'S4'!$B$6:$B$22,$A24,'S4'!$E$6:$E$22,"Diego")+SUMIFS('S4'!$I$6:$I$22,'S4'!$B$6:$B$22,$A24,'S4'!$E$6:$E$22,"Ambos")+SUMIFS('S5'!$I$6:$I$20,'S5'!$B$6:$B$20,$A24,'S5'!$E$6:$E$20,"Diego")+SUMIFS('S5'!$I$6:$I$20,'S5'!$B$6:$B$20,$A24,'S5'!$E$6:$E$20,"Ambos")+SUMIFS('S6'!$I$6:$I$17,'S6'!$B$6:$B$17,$A24,'S6'!$E$6:$E$17,"Diego")+SUMIFS('S6'!$I$6:$I$17,'S6'!$B$6:$B$17,$A24,'S6'!$E$6:$E$17,"Ambos")+SUMIFS('S7'!$I$6:$I$19,'S7'!$B$6:$B$19,$A24,'S7'!$E$6:$E$19,"Diego")+SUMIFS('S7'!$I$6:$I$19,'S7'!$B$6:$B$19,$A24,'S7'!$E$6:$E$19,"Ambos")+SUMIFS('S8'!$I$6:$I$23,'S8'!$B$6:$B$23,$A24,'S8'!$E$6:$E$23,"Diego")+SUMIFS('S8'!$I$6:$I$23,'S8'!$B$6:$B$23,$A24,'S8'!$E$6:$E$23,"Ambos")+SUMIFS('S9'!$I$6:$I$15,'S9'!$B$6:$B$15,$A24,'S9'!$E$6:$E$15,"Diego")+SUMIFS('S9'!$I$6:$I$15,'S9'!$B$6:$B$15,$A24,'S9'!$E$6:$E$15,"Ambos")+SUMIFS('S10'!$I$6:$I$13,'S10'!$B$6:$B$13,$A24,'S10'!$E$6:$E$13,"Diego")+SUMIFS('S10'!$I$6:$I$13,'S10'!$B$6:$B$13,$A24,'S10'!$E$6:$E$13,"Ambos")+SUMIFS('Holgura'!$I$6:$I$11,'Holgura'!$B$6:$B$11,$A24,'Holgura'!$E$6:$E$11,"Diego")+SUMIFS('Holgura'!$I$6:$I$11,'Holgura'!$B$6:$B$11,$A24,'Holgura'!$E$6:$E$11,"Ambos")+SUMIFS('Entrega'!$I$6:$I$9,'Entrega'!$B$6:$B$9,$A24,'Entrega'!$E$6:$E$9,"Diego")+SUMIFS('Entrega'!$I$6:$I$9,'Entrega'!$B$6:$B$9,$A24,'Entrega'!$E$6:$E$9,"Ambos")+SUMIFS('Defensa'!$I$6:$I$10,'Defensa'!$B$6:$B$10,$A24,'Defensa'!$E$6:$E$10,"Diego")+SUMIFS('Defensa'!$I$6:$I$10,'Defensa'!$B$6:$B$10,$A24,'Defensa'!$E$6:$E$10,"Ambos")</f>
         <v/>
       </c>
       <c r="F24" s="21">
-        <f>COUNTIFS('S1'!$B$6:$B$32,$A24,'S1'!$E$6:$E$32,"Víctor")+COUNTIFS('S1'!$B$6:$B$32,$A24,'S1'!$E$6:$E$32,"Ambos")+COUNTIFS('S2'!$B$6:$B$23,$A24,'S2'!$E$6:$E$23,"Víctor")+COUNTIFS('S2'!$B$6:$B$23,$A24,'S2'!$E$6:$E$23,"Ambos")+COUNTIFS('S3'!$B$6:$B$19,$A24,'S3'!$E$6:$E$19,"Víctor")+COUNTIFS('S3'!$B$6:$B$19,$A24,'S3'!$E$6:$E$19,"Ambos")+COUNTIFS('S4'!$B$6:$B$20,$A24,'S4'!$E$6:$E$20,"Víctor")+COUNTIFS('S4'!$B$6:$B$20,$A24,'S4'!$E$6:$E$20,"Ambos")+COUNTIFS('S5'!$B$6:$B$20,$A24,'S5'!$E$6:$E$20,"Víctor")+COUNTIFS('S5'!$B$6:$B$20,$A24,'S5'!$E$6:$E$20,"Ambos")+COUNTIFS('S6'!$B$6:$B$17,$A24,'S6'!$E$6:$E$17,"Víctor")+COUNTIFS('S6'!$B$6:$B$17,$A24,'S6'!$E$6:$E$17,"Ambos")+COUNTIFS('S7'!$B$6:$B$19,$A24,'S7'!$E$6:$E$19,"Víctor")+COUNTIFS('S7'!$B$6:$B$19,$A24,'S7'!$E$6:$E$19,"Ambos")+COUNTIFS('S8'!$B$6:$B$23,$A24,'S8'!$E$6:$E$23,"Víctor")+COUNTIFS('S8'!$B$6:$B$23,$A24,'S8'!$E$6:$E$23,"Ambos")+COUNTIFS('S9'!$B$6:$B$15,$A24,'S9'!$E$6:$E$15,"Víctor")+COUNTIFS('S9'!$B$6:$B$15,$A24,'S9'!$E$6:$E$15,"Ambos")+COUNTIFS('S10'!$B$6:$B$13,$A24,'S10'!$E$6:$E$13,"Víctor")+COUNTIFS('S10'!$B$6:$B$13,$A24,'S10'!$E$6:$E$13,"Ambos")+COUNTIFS('Holgura'!$B$6:$B$11,$A24,'Holgura'!$E$6:$E$11,"Víctor")+COUNTIFS('Holgura'!$B$6:$B$11,$A24,'Holgura'!$E$6:$E$11,"Ambos")+COUNTIFS('Entrega'!$B$6:$B$9,$A24,'Entrega'!$E$6:$E$9,"Víctor")+COUNTIFS('Entrega'!$B$6:$B$9,$A24,'Entrega'!$E$6:$E$9,"Ambos")+COUNTIFS('Defensa'!$B$6:$B$10,$A24,'Defensa'!$E$6:$E$10,"Víctor")+COUNTIFS('Defensa'!$B$6:$B$10,$A24,'Defensa'!$E$6:$E$10,"Ambos")</f>
+        <f>COUNTIFS('S1'!$B$6:$B$32,$A24,'S1'!$E$6:$E$32,"Víctor")+COUNTIFS('S1'!$B$6:$B$32,$A24,'S1'!$E$6:$E$32,"Ambos")+COUNTIFS('S2'!$B$6:$B$23,$A24,'S2'!$E$6:$E$23,"Víctor")+COUNTIFS('S2'!$B$6:$B$23,$A24,'S2'!$E$6:$E$23,"Ambos")+COUNTIFS('S3'!$B$6:$B$24,$A24,'S3'!$E$6:$E$24,"Víctor")+COUNTIFS('S3'!$B$6:$B$24,$A24,'S3'!$E$6:$E$24,"Ambos")+COUNTIFS('S4'!$B$6:$B$22,$A24,'S4'!$E$6:$E$22,"Víctor")+COUNTIFS('S4'!$B$6:$B$22,$A24,'S4'!$E$6:$E$22,"Ambos")+COUNTIFS('S5'!$B$6:$B$20,$A24,'S5'!$E$6:$E$20,"Víctor")+COUNTIFS('S5'!$B$6:$B$20,$A24,'S5'!$E$6:$E$20,"Ambos")+COUNTIFS('S6'!$B$6:$B$17,$A24,'S6'!$E$6:$E$17,"Víctor")+COUNTIFS('S6'!$B$6:$B$17,$A24,'S6'!$E$6:$E$17,"Ambos")+COUNTIFS('S7'!$B$6:$B$19,$A24,'S7'!$E$6:$E$19,"Víctor")+COUNTIFS('S7'!$B$6:$B$19,$A24,'S7'!$E$6:$E$19,"Ambos")+COUNTIFS('S8'!$B$6:$B$23,$A24,'S8'!$E$6:$E$23,"Víctor")+COUNTIFS('S8'!$B$6:$B$23,$A24,'S8'!$E$6:$E$23,"Ambos")+COUNTIFS('S9'!$B$6:$B$15,$A24,'S9'!$E$6:$E$15,"Víctor")+COUNTIFS('S9'!$B$6:$B$15,$A24,'S9'!$E$6:$E$15,"Ambos")+COUNTIFS('S10'!$B$6:$B$13,$A24,'S10'!$E$6:$E$13,"Víctor")+COUNTIFS('S10'!$B$6:$B$13,$A24,'S10'!$E$6:$E$13,"Ambos")+COUNTIFS('Holgura'!$B$6:$B$11,$A24,'Holgura'!$E$6:$E$11,"Víctor")+COUNTIFS('Holgura'!$B$6:$B$11,$A24,'Holgura'!$E$6:$E$11,"Ambos")+COUNTIFS('Entrega'!$B$6:$B$9,$A24,'Entrega'!$E$6:$E$9,"Víctor")+COUNTIFS('Entrega'!$B$6:$B$9,$A24,'Entrega'!$E$6:$E$9,"Ambos")+COUNTIFS('Defensa'!$B$6:$B$10,$A24,'Defensa'!$E$6:$E$10,"Víctor")+COUNTIFS('Defensa'!$B$6:$B$10,$A24,'Defensa'!$E$6:$E$10,"Ambos")</f>
         <v/>
       </c>
       <c r="G24" s="21">
-        <f>COUNTIFS('S1'!$B$6:$B$32,$A24,'S1'!$E$6:$E$32,"Diego")+COUNTIFS('S1'!$B$6:$B$32,$A24,'S1'!$E$6:$E$32,"Ambos")+COUNTIFS('S2'!$B$6:$B$23,$A24,'S2'!$E$6:$E$23,"Diego")+COUNTIFS('S2'!$B$6:$B$23,$A24,'S2'!$E$6:$E$23,"Ambos")+COUNTIFS('S3'!$B$6:$B$19,$A24,'S3'!$E$6:$E$19,"Diego")+COUNTIFS('S3'!$B$6:$B$19,$A24,'S3'!$E$6:$E$19,"Ambos")+COUNTIFS('S4'!$B$6:$B$20,$A24,'S4'!$E$6:$E$20,"Diego")+COUNTIFS('S4'!$B$6:$B$20,$A24,'S4'!$E$6:$E$20,"Ambos")+COUNTIFS('S5'!$B$6:$B$20,$A24,'S5'!$E$6:$E$20,"Diego")+COUNTIFS('S5'!$B$6:$B$20,$A24,'S5'!$E$6:$E$20,"Ambos")+COUNTIFS('S6'!$B$6:$B$17,$A24,'S6'!$E$6:$E$17,"Diego")+COUNTIFS('S6'!$B$6:$B$17,$A24,'S6'!$E$6:$E$17,"Ambos")+COUNTIFS('S7'!$B$6:$B$19,$A24,'S7'!$E$6:$E$19,"Diego")+COUNTIFS('S7'!$B$6:$B$19,$A24,'S7'!$E$6:$E$19,"Ambos")+COUNTIFS('S8'!$B$6:$B$23,$A24,'S8'!$E$6:$E$23,"Diego")+COUNTIFS('S8'!$B$6:$B$23,$A24,'S8'!$E$6:$E$23,"Ambos")+COUNTIFS('S9'!$B$6:$B$15,$A24,'S9'!$E$6:$E$15,"Diego")+COUNTIFS('S9'!$B$6:$B$15,$A24,'S9'!$E$6:$E$15,"Ambos")+COUNTIFS('S10'!$B$6:$B$13,$A24,'S10'!$E$6:$E$13,"Diego")+COUNTIFS('S10'!$B$6:$B$13,$A24,'S10'!$E$6:$E$13,"Ambos")+COUNTIFS('Holgura'!$B$6:$B$11,$A24,'Holgura'!$E$6:$E$11,"Diego")+COUNTIFS('Holgura'!$B$6:$B$11,$A24,'Holgura'!$E$6:$E$11,"Ambos")+COUNTIFS('Entrega'!$B$6:$B$9,$A24,'Entrega'!$E$6:$E$9,"Diego")+COUNTIFS('Entrega'!$B$6:$B$9,$A24,'Entrega'!$E$6:$E$9,"Ambos")+COUNTIFS('Defensa'!$B$6:$B$10,$A24,'Defensa'!$E$6:$E$10,"Diego")+COUNTIFS('Defensa'!$B$6:$B$10,$A24,'Defensa'!$E$6:$E$10,"Ambos")</f>
+        <f>COUNTIFS('S1'!$B$6:$B$32,$A24,'S1'!$E$6:$E$32,"Diego")+COUNTIFS('S1'!$B$6:$B$32,$A24,'S1'!$E$6:$E$32,"Ambos")+COUNTIFS('S2'!$B$6:$B$23,$A24,'S2'!$E$6:$E$23,"Diego")+COUNTIFS('S2'!$B$6:$B$23,$A24,'S2'!$E$6:$E$23,"Ambos")+COUNTIFS('S3'!$B$6:$B$24,$A24,'S3'!$E$6:$E$24,"Diego")+COUNTIFS('S3'!$B$6:$B$24,$A24,'S3'!$E$6:$E$24,"Ambos")+COUNTIFS('S4'!$B$6:$B$22,$A24,'S4'!$E$6:$E$22,"Diego")+COUNTIFS('S4'!$B$6:$B$22,$A24,'S4'!$E$6:$E$22,"Ambos")+COUNTIFS('S5'!$B$6:$B$20,$A24,'S5'!$E$6:$E$20,"Diego")+COUNTIFS('S5'!$B$6:$B$20,$A24,'S5'!$E$6:$E$20,"Ambos")+COUNTIFS('S6'!$B$6:$B$17,$A24,'S6'!$E$6:$E$17,"Diego")+COUNTIFS('S6'!$B$6:$B$17,$A24,'S6'!$E$6:$E$17,"Ambos")+COUNTIFS('S7'!$B$6:$B$19,$A24,'S7'!$E$6:$E$19,"Diego")+COUNTIFS('S7'!$B$6:$B$19,$A24,'S7'!$E$6:$E$19,"Ambos")+COUNTIFS('S8'!$B$6:$B$23,$A24,'S8'!$E$6:$E$23,"Diego")+COUNTIFS('S8'!$B$6:$B$23,$A24,'S8'!$E$6:$E$23,"Ambos")+COUNTIFS('S9'!$B$6:$B$15,$A24,'S9'!$E$6:$E$15,"Diego")+COUNTIFS('S9'!$B$6:$B$15,$A24,'S9'!$E$6:$E$15,"Ambos")+COUNTIFS('S10'!$B$6:$B$13,$A24,'S10'!$E$6:$E$13,"Diego")+COUNTIFS('S10'!$B$6:$B$13,$A24,'S10'!$E$6:$E$13,"Ambos")+COUNTIFS('Holgura'!$B$6:$B$11,$A24,'Holgura'!$E$6:$E$11,"Diego")+COUNTIFS('Holgura'!$B$6:$B$11,$A24,'Holgura'!$E$6:$E$11,"Ambos")+COUNTIFS('Entrega'!$B$6:$B$9,$A24,'Entrega'!$E$6:$E$9,"Diego")+COUNTIFS('Entrega'!$B$6:$B$9,$A24,'Entrega'!$E$6:$E$9,"Ambos")+COUNTIFS('Defensa'!$B$6:$B$10,$A24,'Defensa'!$E$6:$E$10,"Diego")+COUNTIFS('Defensa'!$B$6:$B$10,$A24,'Defensa'!$E$6:$E$10,"Ambos")</f>
         <v/>
       </c>
     </row>
@@ -9260,19 +9281,19 @@
         <v/>
       </c>
       <c r="D25" s="21">
-        <f>SUMIFS('S1'!$I$6:$I$32,'S1'!$B$6:$B$32,$A25,'S1'!$E$6:$E$32,"Víctor")+SUMIFS('S1'!$I$6:$I$32,'S1'!$B$6:$B$32,$A25,'S1'!$E$6:$E$32,"Ambos")+SUMIFS('S2'!$I$6:$I$23,'S2'!$B$6:$B$23,$A25,'S2'!$E$6:$E$23,"Víctor")+SUMIFS('S2'!$I$6:$I$23,'S2'!$B$6:$B$23,$A25,'S2'!$E$6:$E$23,"Ambos")+SUMIFS('S3'!$I$6:$I$19,'S3'!$B$6:$B$19,$A25,'S3'!$E$6:$E$19,"Víctor")+SUMIFS('S3'!$I$6:$I$19,'S3'!$B$6:$B$19,$A25,'S3'!$E$6:$E$19,"Ambos")+SUMIFS('S4'!$I$6:$I$20,'S4'!$B$6:$B$20,$A25,'S4'!$E$6:$E$20,"Víctor")+SUMIFS('S4'!$I$6:$I$20,'S4'!$B$6:$B$20,$A25,'S4'!$E$6:$E$20,"Ambos")+SUMIFS('S5'!$I$6:$I$20,'S5'!$B$6:$B$20,$A25,'S5'!$E$6:$E$20,"Víctor")+SUMIFS('S5'!$I$6:$I$20,'S5'!$B$6:$B$20,$A25,'S5'!$E$6:$E$20,"Ambos")+SUMIFS('S6'!$I$6:$I$17,'S6'!$B$6:$B$17,$A25,'S6'!$E$6:$E$17,"Víctor")+SUMIFS('S6'!$I$6:$I$17,'S6'!$B$6:$B$17,$A25,'S6'!$E$6:$E$17,"Ambos")+SUMIFS('S7'!$I$6:$I$19,'S7'!$B$6:$B$19,$A25,'S7'!$E$6:$E$19,"Víctor")+SUMIFS('S7'!$I$6:$I$19,'S7'!$B$6:$B$19,$A25,'S7'!$E$6:$E$19,"Ambos")+SUMIFS('S8'!$I$6:$I$23,'S8'!$B$6:$B$23,$A25,'S8'!$E$6:$E$23,"Víctor")+SUMIFS('S8'!$I$6:$I$23,'S8'!$B$6:$B$23,$A25,'S8'!$E$6:$E$23,"Ambos")+SUMIFS('S9'!$I$6:$I$15,'S9'!$B$6:$B$15,$A25,'S9'!$E$6:$E$15,"Víctor")+SUMIFS('S9'!$I$6:$I$15,'S9'!$B$6:$B$15,$A25,'S9'!$E$6:$E$15,"Ambos")+SUMIFS('S10'!$I$6:$I$13,'S10'!$B$6:$B$13,$A25,'S10'!$E$6:$E$13,"Víctor")+SUMIFS('S10'!$I$6:$I$13,'S10'!$B$6:$B$13,$A25,'S10'!$E$6:$E$13,"Ambos")+SUMIFS('Holgura'!$I$6:$I$11,'Holgura'!$B$6:$B$11,$A25,'Holgura'!$E$6:$E$11,"Víctor")+SUMIFS('Holgura'!$I$6:$I$11,'Holgura'!$B$6:$B$11,$A25,'Holgura'!$E$6:$E$11,"Ambos")+SUMIFS('Entrega'!$I$6:$I$9,'Entrega'!$B$6:$B$9,$A25,'Entrega'!$E$6:$E$9,"Víctor")+SUMIFS('Entrega'!$I$6:$I$9,'Entrega'!$B$6:$B$9,$A25,'Entrega'!$E$6:$E$9,"Ambos")+SUMIFS('Defensa'!$I$6:$I$10,'Defensa'!$B$6:$B$10,$A25,'Defensa'!$E$6:$E$10,"Víctor")+SUMIFS('Defensa'!$I$6:$I$10,'Defensa'!$B$6:$B$10,$A25,'Defensa'!$E$6:$E$10,"Ambos")</f>
+        <f>SUMIFS('S1'!$I$6:$I$32,'S1'!$B$6:$B$32,$A25,'S1'!$E$6:$E$32,"Víctor")+SUMIFS('S1'!$I$6:$I$32,'S1'!$B$6:$B$32,$A25,'S1'!$E$6:$E$32,"Ambos")+SUMIFS('S2'!$I$6:$I$23,'S2'!$B$6:$B$23,$A25,'S2'!$E$6:$E$23,"Víctor")+SUMIFS('S2'!$I$6:$I$23,'S2'!$B$6:$B$23,$A25,'S2'!$E$6:$E$23,"Ambos")+SUMIFS('S3'!$I$6:$I$24,'S3'!$B$6:$B$24,$A25,'S3'!$E$6:$E$24,"Víctor")+SUMIFS('S3'!$I$6:$I$24,'S3'!$B$6:$B$24,$A25,'S3'!$E$6:$E$24,"Ambos")+SUMIFS('S4'!$I$6:$I$22,'S4'!$B$6:$B$22,$A25,'S4'!$E$6:$E$22,"Víctor")+SUMIFS('S4'!$I$6:$I$22,'S4'!$B$6:$B$22,$A25,'S4'!$E$6:$E$22,"Ambos")+SUMIFS('S5'!$I$6:$I$20,'S5'!$B$6:$B$20,$A25,'S5'!$E$6:$E$20,"Víctor")+SUMIFS('S5'!$I$6:$I$20,'S5'!$B$6:$B$20,$A25,'S5'!$E$6:$E$20,"Ambos")+SUMIFS('S6'!$I$6:$I$17,'S6'!$B$6:$B$17,$A25,'S6'!$E$6:$E$17,"Víctor")+SUMIFS('S6'!$I$6:$I$17,'S6'!$B$6:$B$17,$A25,'S6'!$E$6:$E$17,"Ambos")+SUMIFS('S7'!$I$6:$I$19,'S7'!$B$6:$B$19,$A25,'S7'!$E$6:$E$19,"Víctor")+SUMIFS('S7'!$I$6:$I$19,'S7'!$B$6:$B$19,$A25,'S7'!$E$6:$E$19,"Ambos")+SUMIFS('S8'!$I$6:$I$23,'S8'!$B$6:$B$23,$A25,'S8'!$E$6:$E$23,"Víctor")+SUMIFS('S8'!$I$6:$I$23,'S8'!$B$6:$B$23,$A25,'S8'!$E$6:$E$23,"Ambos")+SUMIFS('S9'!$I$6:$I$15,'S9'!$B$6:$B$15,$A25,'S9'!$E$6:$E$15,"Víctor")+SUMIFS('S9'!$I$6:$I$15,'S9'!$B$6:$B$15,$A25,'S9'!$E$6:$E$15,"Ambos")+SUMIFS('S10'!$I$6:$I$13,'S10'!$B$6:$B$13,$A25,'S10'!$E$6:$E$13,"Víctor")+SUMIFS('S10'!$I$6:$I$13,'S10'!$B$6:$B$13,$A25,'S10'!$E$6:$E$13,"Ambos")+SUMIFS('Holgura'!$I$6:$I$11,'Holgura'!$B$6:$B$11,$A25,'Holgura'!$E$6:$E$11,"Víctor")+SUMIFS('Holgura'!$I$6:$I$11,'Holgura'!$B$6:$B$11,$A25,'Holgura'!$E$6:$E$11,"Ambos")+SUMIFS('Entrega'!$I$6:$I$9,'Entrega'!$B$6:$B$9,$A25,'Entrega'!$E$6:$E$9,"Víctor")+SUMIFS('Entrega'!$I$6:$I$9,'Entrega'!$B$6:$B$9,$A25,'Entrega'!$E$6:$E$9,"Ambos")+SUMIFS('Defensa'!$I$6:$I$10,'Defensa'!$B$6:$B$10,$A25,'Defensa'!$E$6:$E$10,"Víctor")+SUMIFS('Defensa'!$I$6:$I$10,'Defensa'!$B$6:$B$10,$A25,'Defensa'!$E$6:$E$10,"Ambos")</f>
         <v/>
       </c>
       <c r="E25" s="21">
-        <f>SUMIFS('S1'!$I$6:$I$32,'S1'!$B$6:$B$32,$A25,'S1'!$E$6:$E$32,"Diego")+SUMIFS('S1'!$I$6:$I$32,'S1'!$B$6:$B$32,$A25,'S1'!$E$6:$E$32,"Ambos")+SUMIFS('S2'!$I$6:$I$23,'S2'!$B$6:$B$23,$A25,'S2'!$E$6:$E$23,"Diego")+SUMIFS('S2'!$I$6:$I$23,'S2'!$B$6:$B$23,$A25,'S2'!$E$6:$E$23,"Ambos")+SUMIFS('S3'!$I$6:$I$19,'S3'!$B$6:$B$19,$A25,'S3'!$E$6:$E$19,"Diego")+SUMIFS('S3'!$I$6:$I$19,'S3'!$B$6:$B$19,$A25,'S3'!$E$6:$E$19,"Ambos")+SUMIFS('S4'!$I$6:$I$20,'S4'!$B$6:$B$20,$A25,'S4'!$E$6:$E$20,"Diego")+SUMIFS('S4'!$I$6:$I$20,'S4'!$B$6:$B$20,$A25,'S4'!$E$6:$E$20,"Ambos")+SUMIFS('S5'!$I$6:$I$20,'S5'!$B$6:$B$20,$A25,'S5'!$E$6:$E$20,"Diego")+SUMIFS('S5'!$I$6:$I$20,'S5'!$B$6:$B$20,$A25,'S5'!$E$6:$E$20,"Ambos")+SUMIFS('S6'!$I$6:$I$17,'S6'!$B$6:$B$17,$A25,'S6'!$E$6:$E$17,"Diego")+SUMIFS('S6'!$I$6:$I$17,'S6'!$B$6:$B$17,$A25,'S6'!$E$6:$E$17,"Ambos")+SUMIFS('S7'!$I$6:$I$19,'S7'!$B$6:$B$19,$A25,'S7'!$E$6:$E$19,"Diego")+SUMIFS('S7'!$I$6:$I$19,'S7'!$B$6:$B$19,$A25,'S7'!$E$6:$E$19,"Ambos")+SUMIFS('S8'!$I$6:$I$23,'S8'!$B$6:$B$23,$A25,'S8'!$E$6:$E$23,"Diego")+SUMIFS('S8'!$I$6:$I$23,'S8'!$B$6:$B$23,$A25,'S8'!$E$6:$E$23,"Ambos")+SUMIFS('S9'!$I$6:$I$15,'S9'!$B$6:$B$15,$A25,'S9'!$E$6:$E$15,"Diego")+SUMIFS('S9'!$I$6:$I$15,'S9'!$B$6:$B$15,$A25,'S9'!$E$6:$E$15,"Ambos")+SUMIFS('S10'!$I$6:$I$13,'S10'!$B$6:$B$13,$A25,'S10'!$E$6:$E$13,"Diego")+SUMIFS('S10'!$I$6:$I$13,'S10'!$B$6:$B$13,$A25,'S10'!$E$6:$E$13,"Ambos")+SUMIFS('Holgura'!$I$6:$I$11,'Holgura'!$B$6:$B$11,$A25,'Holgura'!$E$6:$E$11,"Diego")+SUMIFS('Holgura'!$I$6:$I$11,'Holgura'!$B$6:$B$11,$A25,'Holgura'!$E$6:$E$11,"Ambos")+SUMIFS('Entrega'!$I$6:$I$9,'Entrega'!$B$6:$B$9,$A25,'Entrega'!$E$6:$E$9,"Diego")+SUMIFS('Entrega'!$I$6:$I$9,'Entrega'!$B$6:$B$9,$A25,'Entrega'!$E$6:$E$9,"Ambos")+SUMIFS('Defensa'!$I$6:$I$10,'Defensa'!$B$6:$B$10,$A25,'Defensa'!$E$6:$E$10,"Diego")+SUMIFS('Defensa'!$I$6:$I$10,'Defensa'!$B$6:$B$10,$A25,'Defensa'!$E$6:$E$10,"Ambos")</f>
+        <f>SUMIFS('S1'!$I$6:$I$32,'S1'!$B$6:$B$32,$A25,'S1'!$E$6:$E$32,"Diego")+SUMIFS('S1'!$I$6:$I$32,'S1'!$B$6:$B$32,$A25,'S1'!$E$6:$E$32,"Ambos")+SUMIFS('S2'!$I$6:$I$23,'S2'!$B$6:$B$23,$A25,'S2'!$E$6:$E$23,"Diego")+SUMIFS('S2'!$I$6:$I$23,'S2'!$B$6:$B$23,$A25,'S2'!$E$6:$E$23,"Ambos")+SUMIFS('S3'!$I$6:$I$24,'S3'!$B$6:$B$24,$A25,'S3'!$E$6:$E$24,"Diego")+SUMIFS('S3'!$I$6:$I$24,'S3'!$B$6:$B$24,$A25,'S3'!$E$6:$E$24,"Ambos")+SUMIFS('S4'!$I$6:$I$22,'S4'!$B$6:$B$22,$A25,'S4'!$E$6:$E$22,"Diego")+SUMIFS('S4'!$I$6:$I$22,'S4'!$B$6:$B$22,$A25,'S4'!$E$6:$E$22,"Ambos")+SUMIFS('S5'!$I$6:$I$20,'S5'!$B$6:$B$20,$A25,'S5'!$E$6:$E$20,"Diego")+SUMIFS('S5'!$I$6:$I$20,'S5'!$B$6:$B$20,$A25,'S5'!$E$6:$E$20,"Ambos")+SUMIFS('S6'!$I$6:$I$17,'S6'!$B$6:$B$17,$A25,'S6'!$E$6:$E$17,"Diego")+SUMIFS('S6'!$I$6:$I$17,'S6'!$B$6:$B$17,$A25,'S6'!$E$6:$E$17,"Ambos")+SUMIFS('S7'!$I$6:$I$19,'S7'!$B$6:$B$19,$A25,'S7'!$E$6:$E$19,"Diego")+SUMIFS('S7'!$I$6:$I$19,'S7'!$B$6:$B$19,$A25,'S7'!$E$6:$E$19,"Ambos")+SUMIFS('S8'!$I$6:$I$23,'S8'!$B$6:$B$23,$A25,'S8'!$E$6:$E$23,"Diego")+SUMIFS('S8'!$I$6:$I$23,'S8'!$B$6:$B$23,$A25,'S8'!$E$6:$E$23,"Ambos")+SUMIFS('S9'!$I$6:$I$15,'S9'!$B$6:$B$15,$A25,'S9'!$E$6:$E$15,"Diego")+SUMIFS('S9'!$I$6:$I$15,'S9'!$B$6:$B$15,$A25,'S9'!$E$6:$E$15,"Ambos")+SUMIFS('S10'!$I$6:$I$13,'S10'!$B$6:$B$13,$A25,'S10'!$E$6:$E$13,"Diego")+SUMIFS('S10'!$I$6:$I$13,'S10'!$B$6:$B$13,$A25,'S10'!$E$6:$E$13,"Ambos")+SUMIFS('Holgura'!$I$6:$I$11,'Holgura'!$B$6:$B$11,$A25,'Holgura'!$E$6:$E$11,"Diego")+SUMIFS('Holgura'!$I$6:$I$11,'Holgura'!$B$6:$B$11,$A25,'Holgura'!$E$6:$E$11,"Ambos")+SUMIFS('Entrega'!$I$6:$I$9,'Entrega'!$B$6:$B$9,$A25,'Entrega'!$E$6:$E$9,"Diego")+SUMIFS('Entrega'!$I$6:$I$9,'Entrega'!$B$6:$B$9,$A25,'Entrega'!$E$6:$E$9,"Ambos")+SUMIFS('Defensa'!$I$6:$I$10,'Defensa'!$B$6:$B$10,$A25,'Defensa'!$E$6:$E$10,"Diego")+SUMIFS('Defensa'!$I$6:$I$10,'Defensa'!$B$6:$B$10,$A25,'Defensa'!$E$6:$E$10,"Ambos")</f>
         <v/>
       </c>
       <c r="F25" s="21">
-        <f>COUNTIFS('S1'!$B$6:$B$32,$A25,'S1'!$E$6:$E$32,"Víctor")+COUNTIFS('S1'!$B$6:$B$32,$A25,'S1'!$E$6:$E$32,"Ambos")+COUNTIFS('S2'!$B$6:$B$23,$A25,'S2'!$E$6:$E$23,"Víctor")+COUNTIFS('S2'!$B$6:$B$23,$A25,'S2'!$E$6:$E$23,"Ambos")+COUNTIFS('S3'!$B$6:$B$19,$A25,'S3'!$E$6:$E$19,"Víctor")+COUNTIFS('S3'!$B$6:$B$19,$A25,'S3'!$E$6:$E$19,"Ambos")+COUNTIFS('S4'!$B$6:$B$20,$A25,'S4'!$E$6:$E$20,"Víctor")+COUNTIFS('S4'!$B$6:$B$20,$A25,'S4'!$E$6:$E$20,"Ambos")+COUNTIFS('S5'!$B$6:$B$20,$A25,'S5'!$E$6:$E$20,"Víctor")+COUNTIFS('S5'!$B$6:$B$20,$A25,'S5'!$E$6:$E$20,"Ambos")+COUNTIFS('S6'!$B$6:$B$17,$A25,'S6'!$E$6:$E$17,"Víctor")+COUNTIFS('S6'!$B$6:$B$17,$A25,'S6'!$E$6:$E$17,"Ambos")+COUNTIFS('S7'!$B$6:$B$19,$A25,'S7'!$E$6:$E$19,"Víctor")+COUNTIFS('S7'!$B$6:$B$19,$A25,'S7'!$E$6:$E$19,"Ambos")+COUNTIFS('S8'!$B$6:$B$23,$A25,'S8'!$E$6:$E$23,"Víctor")+COUNTIFS('S8'!$B$6:$B$23,$A25,'S8'!$E$6:$E$23,"Ambos")+COUNTIFS('S9'!$B$6:$B$15,$A25,'S9'!$E$6:$E$15,"Víctor")+COUNTIFS('S9'!$B$6:$B$15,$A25,'S9'!$E$6:$E$15,"Ambos")+COUNTIFS('S10'!$B$6:$B$13,$A25,'S10'!$E$6:$E$13,"Víctor")+COUNTIFS('S10'!$B$6:$B$13,$A25,'S10'!$E$6:$E$13,"Ambos")+COUNTIFS('Holgura'!$B$6:$B$11,$A25,'Holgura'!$E$6:$E$11,"Víctor")+COUNTIFS('Holgura'!$B$6:$B$11,$A25,'Holgura'!$E$6:$E$11,"Ambos")+COUNTIFS('Entrega'!$B$6:$B$9,$A25,'Entrega'!$E$6:$E$9,"Víctor")+COUNTIFS('Entrega'!$B$6:$B$9,$A25,'Entrega'!$E$6:$E$9,"Ambos")+COUNTIFS('Defensa'!$B$6:$B$10,$A25,'Defensa'!$E$6:$E$10,"Víctor")+COUNTIFS('Defensa'!$B$6:$B$10,$A25,'Defensa'!$E$6:$E$10,"Ambos")</f>
+        <f>COUNTIFS('S1'!$B$6:$B$32,$A25,'S1'!$E$6:$E$32,"Víctor")+COUNTIFS('S1'!$B$6:$B$32,$A25,'S1'!$E$6:$E$32,"Ambos")+COUNTIFS('S2'!$B$6:$B$23,$A25,'S2'!$E$6:$E$23,"Víctor")+COUNTIFS('S2'!$B$6:$B$23,$A25,'S2'!$E$6:$E$23,"Ambos")+COUNTIFS('S3'!$B$6:$B$24,$A25,'S3'!$E$6:$E$24,"Víctor")+COUNTIFS('S3'!$B$6:$B$24,$A25,'S3'!$E$6:$E$24,"Ambos")+COUNTIFS('S4'!$B$6:$B$22,$A25,'S4'!$E$6:$E$22,"Víctor")+COUNTIFS('S4'!$B$6:$B$22,$A25,'S4'!$E$6:$E$22,"Ambos")+COUNTIFS('S5'!$B$6:$B$20,$A25,'S5'!$E$6:$E$20,"Víctor")+COUNTIFS('S5'!$B$6:$B$20,$A25,'S5'!$E$6:$E$20,"Ambos")+COUNTIFS('S6'!$B$6:$B$17,$A25,'S6'!$E$6:$E$17,"Víctor")+COUNTIFS('S6'!$B$6:$B$17,$A25,'S6'!$E$6:$E$17,"Ambos")+COUNTIFS('S7'!$B$6:$B$19,$A25,'S7'!$E$6:$E$19,"Víctor")+COUNTIFS('S7'!$B$6:$B$19,$A25,'S7'!$E$6:$E$19,"Ambos")+COUNTIFS('S8'!$B$6:$B$23,$A25,'S8'!$E$6:$E$23,"Víctor")+COUNTIFS('S8'!$B$6:$B$23,$A25,'S8'!$E$6:$E$23,"Ambos")+COUNTIFS('S9'!$B$6:$B$15,$A25,'S9'!$E$6:$E$15,"Víctor")+COUNTIFS('S9'!$B$6:$B$15,$A25,'S9'!$E$6:$E$15,"Ambos")+COUNTIFS('S10'!$B$6:$B$13,$A25,'S10'!$E$6:$E$13,"Víctor")+COUNTIFS('S10'!$B$6:$B$13,$A25,'S10'!$E$6:$E$13,"Ambos")+COUNTIFS('Holgura'!$B$6:$B$11,$A25,'Holgura'!$E$6:$E$11,"Víctor")+COUNTIFS('Holgura'!$B$6:$B$11,$A25,'Holgura'!$E$6:$E$11,"Ambos")+COUNTIFS('Entrega'!$B$6:$B$9,$A25,'Entrega'!$E$6:$E$9,"Víctor")+COUNTIFS('Entrega'!$B$6:$B$9,$A25,'Entrega'!$E$6:$E$9,"Ambos")+COUNTIFS('Defensa'!$B$6:$B$10,$A25,'Defensa'!$E$6:$E$10,"Víctor")+COUNTIFS('Defensa'!$B$6:$B$10,$A25,'Defensa'!$E$6:$E$10,"Ambos")</f>
         <v/>
       </c>
       <c r="G25" s="21">
-        <f>COUNTIFS('S1'!$B$6:$B$32,$A25,'S1'!$E$6:$E$32,"Diego")+COUNTIFS('S1'!$B$6:$B$32,$A25,'S1'!$E$6:$E$32,"Ambos")+COUNTIFS('S2'!$B$6:$B$23,$A25,'S2'!$E$6:$E$23,"Diego")+COUNTIFS('S2'!$B$6:$B$23,$A25,'S2'!$E$6:$E$23,"Ambos")+COUNTIFS('S3'!$B$6:$B$19,$A25,'S3'!$E$6:$E$19,"Diego")+COUNTIFS('S3'!$B$6:$B$19,$A25,'S3'!$E$6:$E$19,"Ambos")+COUNTIFS('S4'!$B$6:$B$20,$A25,'S4'!$E$6:$E$20,"Diego")+COUNTIFS('S4'!$B$6:$B$20,$A25,'S4'!$E$6:$E$20,"Ambos")+COUNTIFS('S5'!$B$6:$B$20,$A25,'S5'!$E$6:$E$20,"Diego")+COUNTIFS('S5'!$B$6:$B$20,$A25,'S5'!$E$6:$E$20,"Ambos")+COUNTIFS('S6'!$B$6:$B$17,$A25,'S6'!$E$6:$E$17,"Diego")+COUNTIFS('S6'!$B$6:$B$17,$A25,'S6'!$E$6:$E$17,"Ambos")+COUNTIFS('S7'!$B$6:$B$19,$A25,'S7'!$E$6:$E$19,"Diego")+COUNTIFS('S7'!$B$6:$B$19,$A25,'S7'!$E$6:$E$19,"Ambos")+COUNTIFS('S8'!$B$6:$B$23,$A25,'S8'!$E$6:$E$23,"Diego")+COUNTIFS('S8'!$B$6:$B$23,$A25,'S8'!$E$6:$E$23,"Ambos")+COUNTIFS('S9'!$B$6:$B$15,$A25,'S9'!$E$6:$E$15,"Diego")+COUNTIFS('S9'!$B$6:$B$15,$A25,'S9'!$E$6:$E$15,"Ambos")+COUNTIFS('S10'!$B$6:$B$13,$A25,'S10'!$E$6:$E$13,"Diego")+COUNTIFS('S10'!$B$6:$B$13,$A25,'S10'!$E$6:$E$13,"Ambos")+COUNTIFS('Holgura'!$B$6:$B$11,$A25,'Holgura'!$E$6:$E$11,"Diego")+COUNTIFS('Holgura'!$B$6:$B$11,$A25,'Holgura'!$E$6:$E$11,"Ambos")+COUNTIFS('Entrega'!$B$6:$B$9,$A25,'Entrega'!$E$6:$E$9,"Diego")+COUNTIFS('Entrega'!$B$6:$B$9,$A25,'Entrega'!$E$6:$E$9,"Ambos")+COUNTIFS('Defensa'!$B$6:$B$10,$A25,'Defensa'!$E$6:$E$10,"Diego")+COUNTIFS('Defensa'!$B$6:$B$10,$A25,'Defensa'!$E$6:$E$10,"Ambos")</f>
+        <f>COUNTIFS('S1'!$B$6:$B$32,$A25,'S1'!$E$6:$E$32,"Diego")+COUNTIFS('S1'!$B$6:$B$32,$A25,'S1'!$E$6:$E$32,"Ambos")+COUNTIFS('S2'!$B$6:$B$23,$A25,'S2'!$E$6:$E$23,"Diego")+COUNTIFS('S2'!$B$6:$B$23,$A25,'S2'!$E$6:$E$23,"Ambos")+COUNTIFS('S3'!$B$6:$B$24,$A25,'S3'!$E$6:$E$24,"Diego")+COUNTIFS('S3'!$B$6:$B$24,$A25,'S3'!$E$6:$E$24,"Ambos")+COUNTIFS('S4'!$B$6:$B$22,$A25,'S4'!$E$6:$E$22,"Diego")+COUNTIFS('S4'!$B$6:$B$22,$A25,'S4'!$E$6:$E$22,"Ambos")+COUNTIFS('S5'!$B$6:$B$20,$A25,'S5'!$E$6:$E$20,"Diego")+COUNTIFS('S5'!$B$6:$B$20,$A25,'S5'!$E$6:$E$20,"Ambos")+COUNTIFS('S6'!$B$6:$B$17,$A25,'S6'!$E$6:$E$17,"Diego")+COUNTIFS('S6'!$B$6:$B$17,$A25,'S6'!$E$6:$E$17,"Ambos")+COUNTIFS('S7'!$B$6:$B$19,$A25,'S7'!$E$6:$E$19,"Diego")+COUNTIFS('S7'!$B$6:$B$19,$A25,'S7'!$E$6:$E$19,"Ambos")+COUNTIFS('S8'!$B$6:$B$23,$A25,'S8'!$E$6:$E$23,"Diego")+COUNTIFS('S8'!$B$6:$B$23,$A25,'S8'!$E$6:$E$23,"Ambos")+COUNTIFS('S9'!$B$6:$B$15,$A25,'S9'!$E$6:$E$15,"Diego")+COUNTIFS('S9'!$B$6:$B$15,$A25,'S9'!$E$6:$E$15,"Ambos")+COUNTIFS('S10'!$B$6:$B$13,$A25,'S10'!$E$6:$E$13,"Diego")+COUNTIFS('S10'!$B$6:$B$13,$A25,'S10'!$E$6:$E$13,"Ambos")+COUNTIFS('Holgura'!$B$6:$B$11,$A25,'Holgura'!$E$6:$E$11,"Diego")+COUNTIFS('Holgura'!$B$6:$B$11,$A25,'Holgura'!$E$6:$E$11,"Ambos")+COUNTIFS('Entrega'!$B$6:$B$9,$A25,'Entrega'!$E$6:$E$9,"Diego")+COUNTIFS('Entrega'!$B$6:$B$9,$A25,'Entrega'!$E$6:$E$9,"Ambos")+COUNTIFS('Defensa'!$B$6:$B$10,$A25,'Defensa'!$E$6:$E$10,"Diego")+COUNTIFS('Defensa'!$B$6:$B$10,$A25,'Defensa'!$E$6:$E$10,"Ambos")</f>
         <v/>
       </c>
     </row>
@@ -9289,19 +9310,19 @@
         <v/>
       </c>
       <c r="D26" s="21">
-        <f>SUMIFS('S1'!$I$6:$I$32,'S1'!$B$6:$B$32,$A26,'S1'!$E$6:$E$32,"Víctor")+SUMIFS('S1'!$I$6:$I$32,'S1'!$B$6:$B$32,$A26,'S1'!$E$6:$E$32,"Ambos")+SUMIFS('S2'!$I$6:$I$23,'S2'!$B$6:$B$23,$A26,'S2'!$E$6:$E$23,"Víctor")+SUMIFS('S2'!$I$6:$I$23,'S2'!$B$6:$B$23,$A26,'S2'!$E$6:$E$23,"Ambos")+SUMIFS('S3'!$I$6:$I$19,'S3'!$B$6:$B$19,$A26,'S3'!$E$6:$E$19,"Víctor")+SUMIFS('S3'!$I$6:$I$19,'S3'!$B$6:$B$19,$A26,'S3'!$E$6:$E$19,"Ambos")+SUMIFS('S4'!$I$6:$I$20,'S4'!$B$6:$B$20,$A26,'S4'!$E$6:$E$20,"Víctor")+SUMIFS('S4'!$I$6:$I$20,'S4'!$B$6:$B$20,$A26,'S4'!$E$6:$E$20,"Ambos")+SUMIFS('S5'!$I$6:$I$20,'S5'!$B$6:$B$20,$A26,'S5'!$E$6:$E$20,"Víctor")+SUMIFS('S5'!$I$6:$I$20,'S5'!$B$6:$B$20,$A26,'S5'!$E$6:$E$20,"Ambos")+SUMIFS('S6'!$I$6:$I$17,'S6'!$B$6:$B$17,$A26,'S6'!$E$6:$E$17,"Víctor")+SUMIFS('S6'!$I$6:$I$17,'S6'!$B$6:$B$17,$A26,'S6'!$E$6:$E$17,"Ambos")+SUMIFS('S7'!$I$6:$I$19,'S7'!$B$6:$B$19,$A26,'S7'!$E$6:$E$19,"Víctor")+SUMIFS('S7'!$I$6:$I$19,'S7'!$B$6:$B$19,$A26,'S7'!$E$6:$E$19,"Ambos")+SUMIFS('S8'!$I$6:$I$23,'S8'!$B$6:$B$23,$A26,'S8'!$E$6:$E$23,"Víctor")+SUMIFS('S8'!$I$6:$I$23,'S8'!$B$6:$B$23,$A26,'S8'!$E$6:$E$23,"Ambos")+SUMIFS('S9'!$I$6:$I$15,'S9'!$B$6:$B$15,$A26,'S9'!$E$6:$E$15,"Víctor")+SUMIFS('S9'!$I$6:$I$15,'S9'!$B$6:$B$15,$A26,'S9'!$E$6:$E$15,"Ambos")+SUMIFS('S10'!$I$6:$I$13,'S10'!$B$6:$B$13,$A26,'S10'!$E$6:$E$13,"Víctor")+SUMIFS('S10'!$I$6:$I$13,'S10'!$B$6:$B$13,$A26,'S10'!$E$6:$E$13,"Ambos")+SUMIFS('Holgura'!$I$6:$I$11,'Holgura'!$B$6:$B$11,$A26,'Holgura'!$E$6:$E$11,"Víctor")+SUMIFS('Holgura'!$I$6:$I$11,'Holgura'!$B$6:$B$11,$A26,'Holgura'!$E$6:$E$11,"Ambos")+SUMIFS('Entrega'!$I$6:$I$9,'Entrega'!$B$6:$B$9,$A26,'Entrega'!$E$6:$E$9,"Víctor")+SUMIFS('Entrega'!$I$6:$I$9,'Entrega'!$B$6:$B$9,$A26,'Entrega'!$E$6:$E$9,"Ambos")+SUMIFS('Defensa'!$I$6:$I$10,'Defensa'!$B$6:$B$10,$A26,'Defensa'!$E$6:$E$10,"Víctor")+SUMIFS('Defensa'!$I$6:$I$10,'Defensa'!$B$6:$B$10,$A26,'Defensa'!$E$6:$E$10,"Ambos")</f>
+        <f>SUMIFS('S1'!$I$6:$I$32,'S1'!$B$6:$B$32,$A26,'S1'!$E$6:$E$32,"Víctor")+SUMIFS('S1'!$I$6:$I$32,'S1'!$B$6:$B$32,$A26,'S1'!$E$6:$E$32,"Ambos")+SUMIFS('S2'!$I$6:$I$23,'S2'!$B$6:$B$23,$A26,'S2'!$E$6:$E$23,"Víctor")+SUMIFS('S2'!$I$6:$I$23,'S2'!$B$6:$B$23,$A26,'S2'!$E$6:$E$23,"Ambos")+SUMIFS('S3'!$I$6:$I$24,'S3'!$B$6:$B$24,$A26,'S3'!$E$6:$E$24,"Víctor")+SUMIFS('S3'!$I$6:$I$24,'S3'!$B$6:$B$24,$A26,'S3'!$E$6:$E$24,"Ambos")+SUMIFS('S4'!$I$6:$I$22,'S4'!$B$6:$B$22,$A26,'S4'!$E$6:$E$22,"Víctor")+SUMIFS('S4'!$I$6:$I$22,'S4'!$B$6:$B$22,$A26,'S4'!$E$6:$E$22,"Ambos")+SUMIFS('S5'!$I$6:$I$20,'S5'!$B$6:$B$20,$A26,'S5'!$E$6:$E$20,"Víctor")+SUMIFS('S5'!$I$6:$I$20,'S5'!$B$6:$B$20,$A26,'S5'!$E$6:$E$20,"Ambos")+SUMIFS('S6'!$I$6:$I$17,'S6'!$B$6:$B$17,$A26,'S6'!$E$6:$E$17,"Víctor")+SUMIFS('S6'!$I$6:$I$17,'S6'!$B$6:$B$17,$A26,'S6'!$E$6:$E$17,"Ambos")+SUMIFS('S7'!$I$6:$I$19,'S7'!$B$6:$B$19,$A26,'S7'!$E$6:$E$19,"Víctor")+SUMIFS('S7'!$I$6:$I$19,'S7'!$B$6:$B$19,$A26,'S7'!$E$6:$E$19,"Ambos")+SUMIFS('S8'!$I$6:$I$23,'S8'!$B$6:$B$23,$A26,'S8'!$E$6:$E$23,"Víctor")+SUMIFS('S8'!$I$6:$I$23,'S8'!$B$6:$B$23,$A26,'S8'!$E$6:$E$23,"Ambos")+SUMIFS('S9'!$I$6:$I$15,'S9'!$B$6:$B$15,$A26,'S9'!$E$6:$E$15,"Víctor")+SUMIFS('S9'!$I$6:$I$15,'S9'!$B$6:$B$15,$A26,'S9'!$E$6:$E$15,"Ambos")+SUMIFS('S10'!$I$6:$I$13,'S10'!$B$6:$B$13,$A26,'S10'!$E$6:$E$13,"Víctor")+SUMIFS('S10'!$I$6:$I$13,'S10'!$B$6:$B$13,$A26,'S10'!$E$6:$E$13,"Ambos")+SUMIFS('Holgura'!$I$6:$I$11,'Holgura'!$B$6:$B$11,$A26,'Holgura'!$E$6:$E$11,"Víctor")+SUMIFS('Holgura'!$I$6:$I$11,'Holgura'!$B$6:$B$11,$A26,'Holgura'!$E$6:$E$11,"Ambos")+SUMIFS('Entrega'!$I$6:$I$9,'Entrega'!$B$6:$B$9,$A26,'Entrega'!$E$6:$E$9,"Víctor")+SUMIFS('Entrega'!$I$6:$I$9,'Entrega'!$B$6:$B$9,$A26,'Entrega'!$E$6:$E$9,"Ambos")+SUMIFS('Defensa'!$I$6:$I$10,'Defensa'!$B$6:$B$10,$A26,'Defensa'!$E$6:$E$10,"Víctor")+SUMIFS('Defensa'!$I$6:$I$10,'Defensa'!$B$6:$B$10,$A26,'Defensa'!$E$6:$E$10,"Ambos")</f>
         <v/>
       </c>
       <c r="E26" s="21">
-        <f>SUMIFS('S1'!$I$6:$I$32,'S1'!$B$6:$B$32,$A26,'S1'!$E$6:$E$32,"Diego")+SUMIFS('S1'!$I$6:$I$32,'S1'!$B$6:$B$32,$A26,'S1'!$E$6:$E$32,"Ambos")+SUMIFS('S2'!$I$6:$I$23,'S2'!$B$6:$B$23,$A26,'S2'!$E$6:$E$23,"Diego")+SUMIFS('S2'!$I$6:$I$23,'S2'!$B$6:$B$23,$A26,'S2'!$E$6:$E$23,"Ambos")+SUMIFS('S3'!$I$6:$I$19,'S3'!$B$6:$B$19,$A26,'S3'!$E$6:$E$19,"Diego")+SUMIFS('S3'!$I$6:$I$19,'S3'!$B$6:$B$19,$A26,'S3'!$E$6:$E$19,"Ambos")+SUMIFS('S4'!$I$6:$I$20,'S4'!$B$6:$B$20,$A26,'S4'!$E$6:$E$20,"Diego")+SUMIFS('S4'!$I$6:$I$20,'S4'!$B$6:$B$20,$A26,'S4'!$E$6:$E$20,"Ambos")+SUMIFS('S5'!$I$6:$I$20,'S5'!$B$6:$B$20,$A26,'S5'!$E$6:$E$20,"Diego")+SUMIFS('S5'!$I$6:$I$20,'S5'!$B$6:$B$20,$A26,'S5'!$E$6:$E$20,"Ambos")+SUMIFS('S6'!$I$6:$I$17,'S6'!$B$6:$B$17,$A26,'S6'!$E$6:$E$17,"Diego")+SUMIFS('S6'!$I$6:$I$17,'S6'!$B$6:$B$17,$A26,'S6'!$E$6:$E$17,"Ambos")+SUMIFS('S7'!$I$6:$I$19,'S7'!$B$6:$B$19,$A26,'S7'!$E$6:$E$19,"Diego")+SUMIFS('S7'!$I$6:$I$19,'S7'!$B$6:$B$19,$A26,'S7'!$E$6:$E$19,"Ambos")+SUMIFS('S8'!$I$6:$I$23,'S8'!$B$6:$B$23,$A26,'S8'!$E$6:$E$23,"Diego")+SUMIFS('S8'!$I$6:$I$23,'S8'!$B$6:$B$23,$A26,'S8'!$E$6:$E$23,"Ambos")+SUMIFS('S9'!$I$6:$I$15,'S9'!$B$6:$B$15,$A26,'S9'!$E$6:$E$15,"Diego")+SUMIFS('S9'!$I$6:$I$15,'S9'!$B$6:$B$15,$A26,'S9'!$E$6:$E$15,"Ambos")+SUMIFS('S10'!$I$6:$I$13,'S10'!$B$6:$B$13,$A26,'S10'!$E$6:$E$13,"Diego")+SUMIFS('S10'!$I$6:$I$13,'S10'!$B$6:$B$13,$A26,'S10'!$E$6:$E$13,"Ambos")+SUMIFS('Holgura'!$I$6:$I$11,'Holgura'!$B$6:$B$11,$A26,'Holgura'!$E$6:$E$11,"Diego")+SUMIFS('Holgura'!$I$6:$I$11,'Holgura'!$B$6:$B$11,$A26,'Holgura'!$E$6:$E$11,"Ambos")+SUMIFS('Entrega'!$I$6:$I$9,'Entrega'!$B$6:$B$9,$A26,'Entrega'!$E$6:$E$9,"Diego")+SUMIFS('Entrega'!$I$6:$I$9,'Entrega'!$B$6:$B$9,$A26,'Entrega'!$E$6:$E$9,"Ambos")+SUMIFS('Defensa'!$I$6:$I$10,'Defensa'!$B$6:$B$10,$A26,'Defensa'!$E$6:$E$10,"Diego")+SUMIFS('Defensa'!$I$6:$I$10,'Defensa'!$B$6:$B$10,$A26,'Defensa'!$E$6:$E$10,"Ambos")</f>
+        <f>SUMIFS('S1'!$I$6:$I$32,'S1'!$B$6:$B$32,$A26,'S1'!$E$6:$E$32,"Diego")+SUMIFS('S1'!$I$6:$I$32,'S1'!$B$6:$B$32,$A26,'S1'!$E$6:$E$32,"Ambos")+SUMIFS('S2'!$I$6:$I$23,'S2'!$B$6:$B$23,$A26,'S2'!$E$6:$E$23,"Diego")+SUMIFS('S2'!$I$6:$I$23,'S2'!$B$6:$B$23,$A26,'S2'!$E$6:$E$23,"Ambos")+SUMIFS('S3'!$I$6:$I$24,'S3'!$B$6:$B$24,$A26,'S3'!$E$6:$E$24,"Diego")+SUMIFS('S3'!$I$6:$I$24,'S3'!$B$6:$B$24,$A26,'S3'!$E$6:$E$24,"Ambos")+SUMIFS('S4'!$I$6:$I$22,'S4'!$B$6:$B$22,$A26,'S4'!$E$6:$E$22,"Diego")+SUMIFS('S4'!$I$6:$I$22,'S4'!$B$6:$B$22,$A26,'S4'!$E$6:$E$22,"Ambos")+SUMIFS('S5'!$I$6:$I$20,'S5'!$B$6:$B$20,$A26,'S5'!$E$6:$E$20,"Diego")+SUMIFS('S5'!$I$6:$I$20,'S5'!$B$6:$B$20,$A26,'S5'!$E$6:$E$20,"Ambos")+SUMIFS('S6'!$I$6:$I$17,'S6'!$B$6:$B$17,$A26,'S6'!$E$6:$E$17,"Diego")+SUMIFS('S6'!$I$6:$I$17,'S6'!$B$6:$B$17,$A26,'S6'!$E$6:$E$17,"Ambos")+SUMIFS('S7'!$I$6:$I$19,'S7'!$B$6:$B$19,$A26,'S7'!$E$6:$E$19,"Diego")+SUMIFS('S7'!$I$6:$I$19,'S7'!$B$6:$B$19,$A26,'S7'!$E$6:$E$19,"Ambos")+SUMIFS('S8'!$I$6:$I$23,'S8'!$B$6:$B$23,$A26,'S8'!$E$6:$E$23,"Diego")+SUMIFS('S8'!$I$6:$I$23,'S8'!$B$6:$B$23,$A26,'S8'!$E$6:$E$23,"Ambos")+SUMIFS('S9'!$I$6:$I$15,'S9'!$B$6:$B$15,$A26,'S9'!$E$6:$E$15,"Diego")+SUMIFS('S9'!$I$6:$I$15,'S9'!$B$6:$B$15,$A26,'S9'!$E$6:$E$15,"Ambos")+SUMIFS('S10'!$I$6:$I$13,'S10'!$B$6:$B$13,$A26,'S10'!$E$6:$E$13,"Diego")+SUMIFS('S10'!$I$6:$I$13,'S10'!$B$6:$B$13,$A26,'S10'!$E$6:$E$13,"Ambos")+SUMIFS('Holgura'!$I$6:$I$11,'Holgura'!$B$6:$B$11,$A26,'Holgura'!$E$6:$E$11,"Diego")+SUMIFS('Holgura'!$I$6:$I$11,'Holgura'!$B$6:$B$11,$A26,'Holgura'!$E$6:$E$11,"Ambos")+SUMIFS('Entrega'!$I$6:$I$9,'Entrega'!$B$6:$B$9,$A26,'Entrega'!$E$6:$E$9,"Diego")+SUMIFS('Entrega'!$I$6:$I$9,'Entrega'!$B$6:$B$9,$A26,'Entrega'!$E$6:$E$9,"Ambos")+SUMIFS('Defensa'!$I$6:$I$10,'Defensa'!$B$6:$B$10,$A26,'Defensa'!$E$6:$E$10,"Diego")+SUMIFS('Defensa'!$I$6:$I$10,'Defensa'!$B$6:$B$10,$A26,'Defensa'!$E$6:$E$10,"Ambos")</f>
         <v/>
       </c>
       <c r="F26" s="21">
-        <f>COUNTIFS('S1'!$B$6:$B$32,$A26,'S1'!$E$6:$E$32,"Víctor")+COUNTIFS('S1'!$B$6:$B$32,$A26,'S1'!$E$6:$E$32,"Ambos")+COUNTIFS('S2'!$B$6:$B$23,$A26,'S2'!$E$6:$E$23,"Víctor")+COUNTIFS('S2'!$B$6:$B$23,$A26,'S2'!$E$6:$E$23,"Ambos")+COUNTIFS('S3'!$B$6:$B$19,$A26,'S3'!$E$6:$E$19,"Víctor")+COUNTIFS('S3'!$B$6:$B$19,$A26,'S3'!$E$6:$E$19,"Ambos")+COUNTIFS('S4'!$B$6:$B$20,$A26,'S4'!$E$6:$E$20,"Víctor")+COUNTIFS('S4'!$B$6:$B$20,$A26,'S4'!$E$6:$E$20,"Ambos")+COUNTIFS('S5'!$B$6:$B$20,$A26,'S5'!$E$6:$E$20,"Víctor")+COUNTIFS('S5'!$B$6:$B$20,$A26,'S5'!$E$6:$E$20,"Ambos")+COUNTIFS('S6'!$B$6:$B$17,$A26,'S6'!$E$6:$E$17,"Víctor")+COUNTIFS('S6'!$B$6:$B$17,$A26,'S6'!$E$6:$E$17,"Ambos")+COUNTIFS('S7'!$B$6:$B$19,$A26,'S7'!$E$6:$E$19,"Víctor")+COUNTIFS('S7'!$B$6:$B$19,$A26,'S7'!$E$6:$E$19,"Ambos")+COUNTIFS('S8'!$B$6:$B$23,$A26,'S8'!$E$6:$E$23,"Víctor")+COUNTIFS('S8'!$B$6:$B$23,$A26,'S8'!$E$6:$E$23,"Ambos")+COUNTIFS('S9'!$B$6:$B$15,$A26,'S9'!$E$6:$E$15,"Víctor")+COUNTIFS('S9'!$B$6:$B$15,$A26,'S9'!$E$6:$E$15,"Ambos")+COUNTIFS('S10'!$B$6:$B$13,$A26,'S10'!$E$6:$E$13,"Víctor")+COUNTIFS('S10'!$B$6:$B$13,$A26,'S10'!$E$6:$E$13,"Ambos")+COUNTIFS('Holgura'!$B$6:$B$11,$A26,'Holgura'!$E$6:$E$11,"Víctor")+COUNTIFS('Holgura'!$B$6:$B$11,$A26,'Holgura'!$E$6:$E$11,"Ambos")+COUNTIFS('Entrega'!$B$6:$B$9,$A26,'Entrega'!$E$6:$E$9,"Víctor")+COUNTIFS('Entrega'!$B$6:$B$9,$A26,'Entrega'!$E$6:$E$9,"Ambos")+COUNTIFS('Defensa'!$B$6:$B$10,$A26,'Defensa'!$E$6:$E$10,"Víctor")+COUNTIFS('Defensa'!$B$6:$B$10,$A26,'Defensa'!$E$6:$E$10,"Ambos")</f>
+        <f>COUNTIFS('S1'!$B$6:$B$32,$A26,'S1'!$E$6:$E$32,"Víctor")+COUNTIFS('S1'!$B$6:$B$32,$A26,'S1'!$E$6:$E$32,"Ambos")+COUNTIFS('S2'!$B$6:$B$23,$A26,'S2'!$E$6:$E$23,"Víctor")+COUNTIFS('S2'!$B$6:$B$23,$A26,'S2'!$E$6:$E$23,"Ambos")+COUNTIFS('S3'!$B$6:$B$24,$A26,'S3'!$E$6:$E$24,"Víctor")+COUNTIFS('S3'!$B$6:$B$24,$A26,'S3'!$E$6:$E$24,"Ambos")+COUNTIFS('S4'!$B$6:$B$22,$A26,'S4'!$E$6:$E$22,"Víctor")+COUNTIFS('S4'!$B$6:$B$22,$A26,'S4'!$E$6:$E$22,"Ambos")+COUNTIFS('S5'!$B$6:$B$20,$A26,'S5'!$E$6:$E$20,"Víctor")+COUNTIFS('S5'!$B$6:$B$20,$A26,'S5'!$E$6:$E$20,"Ambos")+COUNTIFS('S6'!$B$6:$B$17,$A26,'S6'!$E$6:$E$17,"Víctor")+COUNTIFS('S6'!$B$6:$B$17,$A26,'S6'!$E$6:$E$17,"Ambos")+COUNTIFS('S7'!$B$6:$B$19,$A26,'S7'!$E$6:$E$19,"Víctor")+COUNTIFS('S7'!$B$6:$B$19,$A26,'S7'!$E$6:$E$19,"Ambos")+COUNTIFS('S8'!$B$6:$B$23,$A26,'S8'!$E$6:$E$23,"Víctor")+COUNTIFS('S8'!$B$6:$B$23,$A26,'S8'!$E$6:$E$23,"Ambos")+COUNTIFS('S9'!$B$6:$B$15,$A26,'S9'!$E$6:$E$15,"Víctor")+COUNTIFS('S9'!$B$6:$B$15,$A26,'S9'!$E$6:$E$15,"Ambos")+COUNTIFS('S10'!$B$6:$B$13,$A26,'S10'!$E$6:$E$13,"Víctor")+COUNTIFS('S10'!$B$6:$B$13,$A26,'S10'!$E$6:$E$13,"Ambos")+COUNTIFS('Holgura'!$B$6:$B$11,$A26,'Holgura'!$E$6:$E$11,"Víctor")+COUNTIFS('Holgura'!$B$6:$B$11,$A26,'Holgura'!$E$6:$E$11,"Ambos")+COUNTIFS('Entrega'!$B$6:$B$9,$A26,'Entrega'!$E$6:$E$9,"Víctor")+COUNTIFS('Entrega'!$B$6:$B$9,$A26,'Entrega'!$E$6:$E$9,"Ambos")+COUNTIFS('Defensa'!$B$6:$B$10,$A26,'Defensa'!$E$6:$E$10,"Víctor")+COUNTIFS('Defensa'!$B$6:$B$10,$A26,'Defensa'!$E$6:$E$10,"Ambos")</f>
         <v/>
       </c>
       <c r="G26" s="21">
-        <f>COUNTIFS('S1'!$B$6:$B$32,$A26,'S1'!$E$6:$E$32,"Diego")+COUNTIFS('S1'!$B$6:$B$32,$A26,'S1'!$E$6:$E$32,"Ambos")+COUNTIFS('S2'!$B$6:$B$23,$A26,'S2'!$E$6:$E$23,"Diego")+COUNTIFS('S2'!$B$6:$B$23,$A26,'S2'!$E$6:$E$23,"Ambos")+COUNTIFS('S3'!$B$6:$B$19,$A26,'S3'!$E$6:$E$19,"Diego")+COUNTIFS('S3'!$B$6:$B$19,$A26,'S3'!$E$6:$E$19,"Ambos")+COUNTIFS('S4'!$B$6:$B$20,$A26,'S4'!$E$6:$E$20,"Diego")+COUNTIFS('S4'!$B$6:$B$20,$A26,'S4'!$E$6:$E$20,"Ambos")+COUNTIFS('S5'!$B$6:$B$20,$A26,'S5'!$E$6:$E$20,"Diego")+COUNTIFS('S5'!$B$6:$B$20,$A26,'S5'!$E$6:$E$20,"Ambos")+COUNTIFS('S6'!$B$6:$B$17,$A26,'S6'!$E$6:$E$17,"Diego")+COUNTIFS('S6'!$B$6:$B$17,$A26,'S6'!$E$6:$E$17,"Ambos")+COUNTIFS('S7'!$B$6:$B$19,$A26,'S7'!$E$6:$E$19,"Diego")+COUNTIFS('S7'!$B$6:$B$19,$A26,'S7'!$E$6:$E$19,"Ambos")+COUNTIFS('S8'!$B$6:$B$23,$A26,'S8'!$E$6:$E$23,"Diego")+COUNTIFS('S8'!$B$6:$B$23,$A26,'S8'!$E$6:$E$23,"Ambos")+COUNTIFS('S9'!$B$6:$B$15,$A26,'S9'!$E$6:$E$15,"Diego")+COUNTIFS('S9'!$B$6:$B$15,$A26,'S9'!$E$6:$E$15,"Ambos")+COUNTIFS('S10'!$B$6:$B$13,$A26,'S10'!$E$6:$E$13,"Diego")+COUNTIFS('S10'!$B$6:$B$13,$A26,'S10'!$E$6:$E$13,"Ambos")+COUNTIFS('Holgura'!$B$6:$B$11,$A26,'Holgura'!$E$6:$E$11,"Diego")+COUNTIFS('Holgura'!$B$6:$B$11,$A26,'Holgura'!$E$6:$E$11,"Ambos")+COUNTIFS('Entrega'!$B$6:$B$9,$A26,'Entrega'!$E$6:$E$9,"Diego")+COUNTIFS('Entrega'!$B$6:$B$9,$A26,'Entrega'!$E$6:$E$9,"Ambos")+COUNTIFS('Defensa'!$B$6:$B$10,$A26,'Defensa'!$E$6:$E$10,"Diego")+COUNTIFS('Defensa'!$B$6:$B$10,$A26,'Defensa'!$E$6:$E$10,"Ambos")</f>
+        <f>COUNTIFS('S1'!$B$6:$B$32,$A26,'S1'!$E$6:$E$32,"Diego")+COUNTIFS('S1'!$B$6:$B$32,$A26,'S1'!$E$6:$E$32,"Ambos")+COUNTIFS('S2'!$B$6:$B$23,$A26,'S2'!$E$6:$E$23,"Diego")+COUNTIFS('S2'!$B$6:$B$23,$A26,'S2'!$E$6:$E$23,"Ambos")+COUNTIFS('S3'!$B$6:$B$24,$A26,'S3'!$E$6:$E$24,"Diego")+COUNTIFS('S3'!$B$6:$B$24,$A26,'S3'!$E$6:$E$24,"Ambos")+COUNTIFS('S4'!$B$6:$B$22,$A26,'S4'!$E$6:$E$22,"Diego")+COUNTIFS('S4'!$B$6:$B$22,$A26,'S4'!$E$6:$E$22,"Ambos")+COUNTIFS('S5'!$B$6:$B$20,$A26,'S5'!$E$6:$E$20,"Diego")+COUNTIFS('S5'!$B$6:$B$20,$A26,'S5'!$E$6:$E$20,"Ambos")+COUNTIFS('S6'!$B$6:$B$17,$A26,'S6'!$E$6:$E$17,"Diego")+COUNTIFS('S6'!$B$6:$B$17,$A26,'S6'!$E$6:$E$17,"Ambos")+COUNTIFS('S7'!$B$6:$B$19,$A26,'S7'!$E$6:$E$19,"Diego")+COUNTIFS('S7'!$B$6:$B$19,$A26,'S7'!$E$6:$E$19,"Ambos")+COUNTIFS('S8'!$B$6:$B$23,$A26,'S8'!$E$6:$E$23,"Diego")+COUNTIFS('S8'!$B$6:$B$23,$A26,'S8'!$E$6:$E$23,"Ambos")+COUNTIFS('S9'!$B$6:$B$15,$A26,'S9'!$E$6:$E$15,"Diego")+COUNTIFS('S9'!$B$6:$B$15,$A26,'S9'!$E$6:$E$15,"Ambos")+COUNTIFS('S10'!$B$6:$B$13,$A26,'S10'!$E$6:$E$13,"Diego")+COUNTIFS('S10'!$B$6:$B$13,$A26,'S10'!$E$6:$E$13,"Ambos")+COUNTIFS('Holgura'!$B$6:$B$11,$A26,'Holgura'!$E$6:$E$11,"Diego")+COUNTIFS('Holgura'!$B$6:$B$11,$A26,'Holgura'!$E$6:$E$11,"Ambos")+COUNTIFS('Entrega'!$B$6:$B$9,$A26,'Entrega'!$E$6:$E$9,"Diego")+COUNTIFS('Entrega'!$B$6:$B$9,$A26,'Entrega'!$E$6:$E$9,"Ambos")+COUNTIFS('Defensa'!$B$6:$B$10,$A26,'Defensa'!$E$6:$E$10,"Diego")+COUNTIFS('Defensa'!$B$6:$B$10,$A26,'Defensa'!$E$6:$E$10,"Ambos")</f>
         <v/>
       </c>
     </row>
@@ -9318,19 +9339,19 @@
         <v/>
       </c>
       <c r="D27" s="21">
-        <f>SUMIFS('S1'!$I$6:$I$32,'S1'!$B$6:$B$32,$A27,'S1'!$E$6:$E$32,"Víctor")+SUMIFS('S1'!$I$6:$I$32,'S1'!$B$6:$B$32,$A27,'S1'!$E$6:$E$32,"Ambos")+SUMIFS('S2'!$I$6:$I$23,'S2'!$B$6:$B$23,$A27,'S2'!$E$6:$E$23,"Víctor")+SUMIFS('S2'!$I$6:$I$23,'S2'!$B$6:$B$23,$A27,'S2'!$E$6:$E$23,"Ambos")+SUMIFS('S3'!$I$6:$I$19,'S3'!$B$6:$B$19,$A27,'S3'!$E$6:$E$19,"Víctor")+SUMIFS('S3'!$I$6:$I$19,'S3'!$B$6:$B$19,$A27,'S3'!$E$6:$E$19,"Ambos")+SUMIFS('S4'!$I$6:$I$20,'S4'!$B$6:$B$20,$A27,'S4'!$E$6:$E$20,"Víctor")+SUMIFS('S4'!$I$6:$I$20,'S4'!$B$6:$B$20,$A27,'S4'!$E$6:$E$20,"Ambos")+SUMIFS('S5'!$I$6:$I$20,'S5'!$B$6:$B$20,$A27,'S5'!$E$6:$E$20,"Víctor")+SUMIFS('S5'!$I$6:$I$20,'S5'!$B$6:$B$20,$A27,'S5'!$E$6:$E$20,"Ambos")+SUMIFS('S6'!$I$6:$I$17,'S6'!$B$6:$B$17,$A27,'S6'!$E$6:$E$17,"Víctor")+SUMIFS('S6'!$I$6:$I$17,'S6'!$B$6:$B$17,$A27,'S6'!$E$6:$E$17,"Ambos")+SUMIFS('S7'!$I$6:$I$19,'S7'!$B$6:$B$19,$A27,'S7'!$E$6:$E$19,"Víctor")+SUMIFS('S7'!$I$6:$I$19,'S7'!$B$6:$B$19,$A27,'S7'!$E$6:$E$19,"Ambos")+SUMIFS('S8'!$I$6:$I$23,'S8'!$B$6:$B$23,$A27,'S8'!$E$6:$E$23,"Víctor")+SUMIFS('S8'!$I$6:$I$23,'S8'!$B$6:$B$23,$A27,'S8'!$E$6:$E$23,"Ambos")+SUMIFS('S9'!$I$6:$I$15,'S9'!$B$6:$B$15,$A27,'S9'!$E$6:$E$15,"Víctor")+SUMIFS('S9'!$I$6:$I$15,'S9'!$B$6:$B$15,$A27,'S9'!$E$6:$E$15,"Ambos")+SUMIFS('S10'!$I$6:$I$13,'S10'!$B$6:$B$13,$A27,'S10'!$E$6:$E$13,"Víctor")+SUMIFS('S10'!$I$6:$I$13,'S10'!$B$6:$B$13,$A27,'S10'!$E$6:$E$13,"Ambos")+SUMIFS('Holgura'!$I$6:$I$11,'Holgura'!$B$6:$B$11,$A27,'Holgura'!$E$6:$E$11,"Víctor")+SUMIFS('Holgura'!$I$6:$I$11,'Holgura'!$B$6:$B$11,$A27,'Holgura'!$E$6:$E$11,"Ambos")+SUMIFS('Entrega'!$I$6:$I$9,'Entrega'!$B$6:$B$9,$A27,'Entrega'!$E$6:$E$9,"Víctor")+SUMIFS('Entrega'!$I$6:$I$9,'Entrega'!$B$6:$B$9,$A27,'Entrega'!$E$6:$E$9,"Ambos")+SUMIFS('Defensa'!$I$6:$I$10,'Defensa'!$B$6:$B$10,$A27,'Defensa'!$E$6:$E$10,"Víctor")+SUMIFS('Defensa'!$I$6:$I$10,'Defensa'!$B$6:$B$10,$A27,'Defensa'!$E$6:$E$10,"Ambos")</f>
+        <f>SUMIFS('S1'!$I$6:$I$32,'S1'!$B$6:$B$32,$A27,'S1'!$E$6:$E$32,"Víctor")+SUMIFS('S1'!$I$6:$I$32,'S1'!$B$6:$B$32,$A27,'S1'!$E$6:$E$32,"Ambos")+SUMIFS('S2'!$I$6:$I$23,'S2'!$B$6:$B$23,$A27,'S2'!$E$6:$E$23,"Víctor")+SUMIFS('S2'!$I$6:$I$23,'S2'!$B$6:$B$23,$A27,'S2'!$E$6:$E$23,"Ambos")+SUMIFS('S3'!$I$6:$I$24,'S3'!$B$6:$B$24,$A27,'S3'!$E$6:$E$24,"Víctor")+SUMIFS('S3'!$I$6:$I$24,'S3'!$B$6:$B$24,$A27,'S3'!$E$6:$E$24,"Ambos")+SUMIFS('S4'!$I$6:$I$22,'S4'!$B$6:$B$22,$A27,'S4'!$E$6:$E$22,"Víctor")+SUMIFS('S4'!$I$6:$I$22,'S4'!$B$6:$B$22,$A27,'S4'!$E$6:$E$22,"Ambos")+SUMIFS('S5'!$I$6:$I$20,'S5'!$B$6:$B$20,$A27,'S5'!$E$6:$E$20,"Víctor")+SUMIFS('S5'!$I$6:$I$20,'S5'!$B$6:$B$20,$A27,'S5'!$E$6:$E$20,"Ambos")+SUMIFS('S6'!$I$6:$I$17,'S6'!$B$6:$B$17,$A27,'S6'!$E$6:$E$17,"Víctor")+SUMIFS('S6'!$I$6:$I$17,'S6'!$B$6:$B$17,$A27,'S6'!$E$6:$E$17,"Ambos")+SUMIFS('S7'!$I$6:$I$19,'S7'!$B$6:$B$19,$A27,'S7'!$E$6:$E$19,"Víctor")+SUMIFS('S7'!$I$6:$I$19,'S7'!$B$6:$B$19,$A27,'S7'!$E$6:$E$19,"Ambos")+SUMIFS('S8'!$I$6:$I$23,'S8'!$B$6:$B$23,$A27,'S8'!$E$6:$E$23,"Víctor")+SUMIFS('S8'!$I$6:$I$23,'S8'!$B$6:$B$23,$A27,'S8'!$E$6:$E$23,"Ambos")+SUMIFS('S9'!$I$6:$I$15,'S9'!$B$6:$B$15,$A27,'S9'!$E$6:$E$15,"Víctor")+SUMIFS('S9'!$I$6:$I$15,'S9'!$B$6:$B$15,$A27,'S9'!$E$6:$E$15,"Ambos")+SUMIFS('S10'!$I$6:$I$13,'S10'!$B$6:$B$13,$A27,'S10'!$E$6:$E$13,"Víctor")+SUMIFS('S10'!$I$6:$I$13,'S10'!$B$6:$B$13,$A27,'S10'!$E$6:$E$13,"Ambos")+SUMIFS('Holgura'!$I$6:$I$11,'Holgura'!$B$6:$B$11,$A27,'Holgura'!$E$6:$E$11,"Víctor")+SUMIFS('Holgura'!$I$6:$I$11,'Holgura'!$B$6:$B$11,$A27,'Holgura'!$E$6:$E$11,"Ambos")+SUMIFS('Entrega'!$I$6:$I$9,'Entrega'!$B$6:$B$9,$A27,'Entrega'!$E$6:$E$9,"Víctor")+SUMIFS('Entrega'!$I$6:$I$9,'Entrega'!$B$6:$B$9,$A27,'Entrega'!$E$6:$E$9,"Ambos")+SUMIFS('Defensa'!$I$6:$I$10,'Defensa'!$B$6:$B$10,$A27,'Defensa'!$E$6:$E$10,"Víctor")+SUMIFS('Defensa'!$I$6:$I$10,'Defensa'!$B$6:$B$10,$A27,'Defensa'!$E$6:$E$10,"Ambos")</f>
         <v/>
       </c>
       <c r="E27" s="21">
-        <f>SUMIFS('S1'!$I$6:$I$32,'S1'!$B$6:$B$32,$A27,'S1'!$E$6:$E$32,"Diego")+SUMIFS('S1'!$I$6:$I$32,'S1'!$B$6:$B$32,$A27,'S1'!$E$6:$E$32,"Ambos")+SUMIFS('S2'!$I$6:$I$23,'S2'!$B$6:$B$23,$A27,'S2'!$E$6:$E$23,"Diego")+SUMIFS('S2'!$I$6:$I$23,'S2'!$B$6:$B$23,$A27,'S2'!$E$6:$E$23,"Ambos")+SUMIFS('S3'!$I$6:$I$19,'S3'!$B$6:$B$19,$A27,'S3'!$E$6:$E$19,"Diego")+SUMIFS('S3'!$I$6:$I$19,'S3'!$B$6:$B$19,$A27,'S3'!$E$6:$E$19,"Ambos")+SUMIFS('S4'!$I$6:$I$20,'S4'!$B$6:$B$20,$A27,'S4'!$E$6:$E$20,"Diego")+SUMIFS('S4'!$I$6:$I$20,'S4'!$B$6:$B$20,$A27,'S4'!$E$6:$E$20,"Ambos")+SUMIFS('S5'!$I$6:$I$20,'S5'!$B$6:$B$20,$A27,'S5'!$E$6:$E$20,"Diego")+SUMIFS('S5'!$I$6:$I$20,'S5'!$B$6:$B$20,$A27,'S5'!$E$6:$E$20,"Ambos")+SUMIFS('S6'!$I$6:$I$17,'S6'!$B$6:$B$17,$A27,'S6'!$E$6:$E$17,"Diego")+SUMIFS('S6'!$I$6:$I$17,'S6'!$B$6:$B$17,$A27,'S6'!$E$6:$E$17,"Ambos")+SUMIFS('S7'!$I$6:$I$19,'S7'!$B$6:$B$19,$A27,'S7'!$E$6:$E$19,"Diego")+SUMIFS('S7'!$I$6:$I$19,'S7'!$B$6:$B$19,$A27,'S7'!$E$6:$E$19,"Ambos")+SUMIFS('S8'!$I$6:$I$23,'S8'!$B$6:$B$23,$A27,'S8'!$E$6:$E$23,"Diego")+SUMIFS('S8'!$I$6:$I$23,'S8'!$B$6:$B$23,$A27,'S8'!$E$6:$E$23,"Ambos")+SUMIFS('S9'!$I$6:$I$15,'S9'!$B$6:$B$15,$A27,'S9'!$E$6:$E$15,"Diego")+SUMIFS('S9'!$I$6:$I$15,'S9'!$B$6:$B$15,$A27,'S9'!$E$6:$E$15,"Ambos")+SUMIFS('S10'!$I$6:$I$13,'S10'!$B$6:$B$13,$A27,'S10'!$E$6:$E$13,"Diego")+SUMIFS('S10'!$I$6:$I$13,'S10'!$B$6:$B$13,$A27,'S10'!$E$6:$E$13,"Ambos")+SUMIFS('Holgura'!$I$6:$I$11,'Holgura'!$B$6:$B$11,$A27,'Holgura'!$E$6:$E$11,"Diego")+SUMIFS('Holgura'!$I$6:$I$11,'Holgura'!$B$6:$B$11,$A27,'Holgura'!$E$6:$E$11,"Ambos")+SUMIFS('Entrega'!$I$6:$I$9,'Entrega'!$B$6:$B$9,$A27,'Entrega'!$E$6:$E$9,"Diego")+SUMIFS('Entrega'!$I$6:$I$9,'Entrega'!$B$6:$B$9,$A27,'Entrega'!$E$6:$E$9,"Ambos")+SUMIFS('Defensa'!$I$6:$I$10,'Defensa'!$B$6:$B$10,$A27,'Defensa'!$E$6:$E$10,"Diego")+SUMIFS('Defensa'!$I$6:$I$10,'Defensa'!$B$6:$B$10,$A27,'Defensa'!$E$6:$E$10,"Ambos")</f>
+        <f>SUMIFS('S1'!$I$6:$I$32,'S1'!$B$6:$B$32,$A27,'S1'!$E$6:$E$32,"Diego")+SUMIFS('S1'!$I$6:$I$32,'S1'!$B$6:$B$32,$A27,'S1'!$E$6:$E$32,"Ambos")+SUMIFS('S2'!$I$6:$I$23,'S2'!$B$6:$B$23,$A27,'S2'!$E$6:$E$23,"Diego")+SUMIFS('S2'!$I$6:$I$23,'S2'!$B$6:$B$23,$A27,'S2'!$E$6:$E$23,"Ambos")+SUMIFS('S3'!$I$6:$I$24,'S3'!$B$6:$B$24,$A27,'S3'!$E$6:$E$24,"Diego")+SUMIFS('S3'!$I$6:$I$24,'S3'!$B$6:$B$24,$A27,'S3'!$E$6:$E$24,"Ambos")+SUMIFS('S4'!$I$6:$I$22,'S4'!$B$6:$B$22,$A27,'S4'!$E$6:$E$22,"Diego")+SUMIFS('S4'!$I$6:$I$22,'S4'!$B$6:$B$22,$A27,'S4'!$E$6:$E$22,"Ambos")+SUMIFS('S5'!$I$6:$I$20,'S5'!$B$6:$B$20,$A27,'S5'!$E$6:$E$20,"Diego")+SUMIFS('S5'!$I$6:$I$20,'S5'!$B$6:$B$20,$A27,'S5'!$E$6:$E$20,"Ambos")+SUMIFS('S6'!$I$6:$I$17,'S6'!$B$6:$B$17,$A27,'S6'!$E$6:$E$17,"Diego")+SUMIFS('S6'!$I$6:$I$17,'S6'!$B$6:$B$17,$A27,'S6'!$E$6:$E$17,"Ambos")+SUMIFS('S7'!$I$6:$I$19,'S7'!$B$6:$B$19,$A27,'S7'!$E$6:$E$19,"Diego")+SUMIFS('S7'!$I$6:$I$19,'S7'!$B$6:$B$19,$A27,'S7'!$E$6:$E$19,"Ambos")+SUMIFS('S8'!$I$6:$I$23,'S8'!$B$6:$B$23,$A27,'S8'!$E$6:$E$23,"Diego")+SUMIFS('S8'!$I$6:$I$23,'S8'!$B$6:$B$23,$A27,'S8'!$E$6:$E$23,"Ambos")+SUMIFS('S9'!$I$6:$I$15,'S9'!$B$6:$B$15,$A27,'S9'!$E$6:$E$15,"Diego")+SUMIFS('S9'!$I$6:$I$15,'S9'!$B$6:$B$15,$A27,'S9'!$E$6:$E$15,"Ambos")+SUMIFS('S10'!$I$6:$I$13,'S10'!$B$6:$B$13,$A27,'S10'!$E$6:$E$13,"Diego")+SUMIFS('S10'!$I$6:$I$13,'S10'!$B$6:$B$13,$A27,'S10'!$E$6:$E$13,"Ambos")+SUMIFS('Holgura'!$I$6:$I$11,'Holgura'!$B$6:$B$11,$A27,'Holgura'!$E$6:$E$11,"Diego")+SUMIFS('Holgura'!$I$6:$I$11,'Holgura'!$B$6:$B$11,$A27,'Holgura'!$E$6:$E$11,"Ambos")+SUMIFS('Entrega'!$I$6:$I$9,'Entrega'!$B$6:$B$9,$A27,'Entrega'!$E$6:$E$9,"Diego")+SUMIFS('Entrega'!$I$6:$I$9,'Entrega'!$B$6:$B$9,$A27,'Entrega'!$E$6:$E$9,"Ambos")+SUMIFS('Defensa'!$I$6:$I$10,'Defensa'!$B$6:$B$10,$A27,'Defensa'!$E$6:$E$10,"Diego")+SUMIFS('Defensa'!$I$6:$I$10,'Defensa'!$B$6:$B$10,$A27,'Defensa'!$E$6:$E$10,"Ambos")</f>
         <v/>
       </c>
       <c r="F27" s="21">
-        <f>COUNTIFS('S1'!$B$6:$B$32,$A27,'S1'!$E$6:$E$32,"Víctor")+COUNTIFS('S1'!$B$6:$B$32,$A27,'S1'!$E$6:$E$32,"Ambos")+COUNTIFS('S2'!$B$6:$B$23,$A27,'S2'!$E$6:$E$23,"Víctor")+COUNTIFS('S2'!$B$6:$B$23,$A27,'S2'!$E$6:$E$23,"Ambos")+COUNTIFS('S3'!$B$6:$B$19,$A27,'S3'!$E$6:$E$19,"Víctor")+COUNTIFS('S3'!$B$6:$B$19,$A27,'S3'!$E$6:$E$19,"Ambos")+COUNTIFS('S4'!$B$6:$B$20,$A27,'S4'!$E$6:$E$20,"Víctor")+COUNTIFS('S4'!$B$6:$B$20,$A27,'S4'!$E$6:$E$20,"Ambos")+COUNTIFS('S5'!$B$6:$B$20,$A27,'S5'!$E$6:$E$20,"Víctor")+COUNTIFS('S5'!$B$6:$B$20,$A27,'S5'!$E$6:$E$20,"Ambos")+COUNTIFS('S6'!$B$6:$B$17,$A27,'S6'!$E$6:$E$17,"Víctor")+COUNTIFS('S6'!$B$6:$B$17,$A27,'S6'!$E$6:$E$17,"Ambos")+COUNTIFS('S7'!$B$6:$B$19,$A27,'S7'!$E$6:$E$19,"Víctor")+COUNTIFS('S7'!$B$6:$B$19,$A27,'S7'!$E$6:$E$19,"Ambos")+COUNTIFS('S8'!$B$6:$B$23,$A27,'S8'!$E$6:$E$23,"Víctor")+COUNTIFS('S8'!$B$6:$B$23,$A27,'S8'!$E$6:$E$23,"Ambos")+COUNTIFS('S9'!$B$6:$B$15,$A27,'S9'!$E$6:$E$15,"Víctor")+COUNTIFS('S9'!$B$6:$B$15,$A27,'S9'!$E$6:$E$15,"Ambos")+COUNTIFS('S10'!$B$6:$B$13,$A27,'S10'!$E$6:$E$13,"Víctor")+COUNTIFS('S10'!$B$6:$B$13,$A27,'S10'!$E$6:$E$13,"Ambos")+COUNTIFS('Holgura'!$B$6:$B$11,$A27,'Holgura'!$E$6:$E$11,"Víctor")+COUNTIFS('Holgura'!$B$6:$B$11,$A27,'Holgura'!$E$6:$E$11,"Ambos")+COUNTIFS('Entrega'!$B$6:$B$9,$A27,'Entrega'!$E$6:$E$9,"Víctor")+COUNTIFS('Entrega'!$B$6:$B$9,$A27,'Entrega'!$E$6:$E$9,"Ambos")+COUNTIFS('Defensa'!$B$6:$B$10,$A27,'Defensa'!$E$6:$E$10,"Víctor")+COUNTIFS('Defensa'!$B$6:$B$10,$A27,'Defensa'!$E$6:$E$10,"Ambos")</f>
+        <f>COUNTIFS('S1'!$B$6:$B$32,$A27,'S1'!$E$6:$E$32,"Víctor")+COUNTIFS('S1'!$B$6:$B$32,$A27,'S1'!$E$6:$E$32,"Ambos")+COUNTIFS('S2'!$B$6:$B$23,$A27,'S2'!$E$6:$E$23,"Víctor")+COUNTIFS('S2'!$B$6:$B$23,$A27,'S2'!$E$6:$E$23,"Ambos")+COUNTIFS('S3'!$B$6:$B$24,$A27,'S3'!$E$6:$E$24,"Víctor")+COUNTIFS('S3'!$B$6:$B$24,$A27,'S3'!$E$6:$E$24,"Ambos")+COUNTIFS('S4'!$B$6:$B$22,$A27,'S4'!$E$6:$E$22,"Víctor")+COUNTIFS('S4'!$B$6:$B$22,$A27,'S4'!$E$6:$E$22,"Ambos")+COUNTIFS('S5'!$B$6:$B$20,$A27,'S5'!$E$6:$E$20,"Víctor")+COUNTIFS('S5'!$B$6:$B$20,$A27,'S5'!$E$6:$E$20,"Ambos")+COUNTIFS('S6'!$B$6:$B$17,$A27,'S6'!$E$6:$E$17,"Víctor")+COUNTIFS('S6'!$B$6:$B$17,$A27,'S6'!$E$6:$E$17,"Ambos")+COUNTIFS('S7'!$B$6:$B$19,$A27,'S7'!$E$6:$E$19,"Víctor")+COUNTIFS('S7'!$B$6:$B$19,$A27,'S7'!$E$6:$E$19,"Ambos")+COUNTIFS('S8'!$B$6:$B$23,$A27,'S8'!$E$6:$E$23,"Víctor")+COUNTIFS('S8'!$B$6:$B$23,$A27,'S8'!$E$6:$E$23,"Ambos")+COUNTIFS('S9'!$B$6:$B$15,$A27,'S9'!$E$6:$E$15,"Víctor")+COUNTIFS('S9'!$B$6:$B$15,$A27,'S9'!$E$6:$E$15,"Ambos")+COUNTIFS('S10'!$B$6:$B$13,$A27,'S10'!$E$6:$E$13,"Víctor")+COUNTIFS('S10'!$B$6:$B$13,$A27,'S10'!$E$6:$E$13,"Ambos")+COUNTIFS('Holgura'!$B$6:$B$11,$A27,'Holgura'!$E$6:$E$11,"Víctor")+COUNTIFS('Holgura'!$B$6:$B$11,$A27,'Holgura'!$E$6:$E$11,"Ambos")+COUNTIFS('Entrega'!$B$6:$B$9,$A27,'Entrega'!$E$6:$E$9,"Víctor")+COUNTIFS('Entrega'!$B$6:$B$9,$A27,'Entrega'!$E$6:$E$9,"Ambos")+COUNTIFS('Defensa'!$B$6:$B$10,$A27,'Defensa'!$E$6:$E$10,"Víctor")+COUNTIFS('Defensa'!$B$6:$B$10,$A27,'Defensa'!$E$6:$E$10,"Ambos")</f>
         <v/>
       </c>
       <c r="G27" s="21">
-        <f>COUNTIFS('S1'!$B$6:$B$32,$A27,'S1'!$E$6:$E$32,"Diego")+COUNTIFS('S1'!$B$6:$B$32,$A27,'S1'!$E$6:$E$32,"Ambos")+COUNTIFS('S2'!$B$6:$B$23,$A27,'S2'!$E$6:$E$23,"Diego")+COUNTIFS('S2'!$B$6:$B$23,$A27,'S2'!$E$6:$E$23,"Ambos")+COUNTIFS('S3'!$B$6:$B$19,$A27,'S3'!$E$6:$E$19,"Diego")+COUNTIFS('S3'!$B$6:$B$19,$A27,'S3'!$E$6:$E$19,"Ambos")+COUNTIFS('S4'!$B$6:$B$20,$A27,'S4'!$E$6:$E$20,"Diego")+COUNTIFS('S4'!$B$6:$B$20,$A27,'S4'!$E$6:$E$20,"Ambos")+COUNTIFS('S5'!$B$6:$B$20,$A27,'S5'!$E$6:$E$20,"Diego")+COUNTIFS('S5'!$B$6:$B$20,$A27,'S5'!$E$6:$E$20,"Ambos")+COUNTIFS('S6'!$B$6:$B$17,$A27,'S6'!$E$6:$E$17,"Diego")+COUNTIFS('S6'!$B$6:$B$17,$A27,'S6'!$E$6:$E$17,"Ambos")+COUNTIFS('S7'!$B$6:$B$19,$A27,'S7'!$E$6:$E$19,"Diego")+COUNTIFS('S7'!$B$6:$B$19,$A27,'S7'!$E$6:$E$19,"Ambos")+COUNTIFS('S8'!$B$6:$B$23,$A27,'S8'!$E$6:$E$23,"Diego")+COUNTIFS('S8'!$B$6:$B$23,$A27,'S8'!$E$6:$E$23,"Ambos")+COUNTIFS('S9'!$B$6:$B$15,$A27,'S9'!$E$6:$E$15,"Diego")+COUNTIFS('S9'!$B$6:$B$15,$A27,'S9'!$E$6:$E$15,"Ambos")+COUNTIFS('S10'!$B$6:$B$13,$A27,'S10'!$E$6:$E$13,"Diego")+COUNTIFS('S10'!$B$6:$B$13,$A27,'S10'!$E$6:$E$13,"Ambos")+COUNTIFS('Holgura'!$B$6:$B$11,$A27,'Holgura'!$E$6:$E$11,"Diego")+COUNTIFS('Holgura'!$B$6:$B$11,$A27,'Holgura'!$E$6:$E$11,"Ambos")+COUNTIFS('Entrega'!$B$6:$B$9,$A27,'Entrega'!$E$6:$E$9,"Diego")+COUNTIFS('Entrega'!$B$6:$B$9,$A27,'Entrega'!$E$6:$E$9,"Ambos")+COUNTIFS('Defensa'!$B$6:$B$10,$A27,'Defensa'!$E$6:$E$10,"Diego")+COUNTIFS('Defensa'!$B$6:$B$10,$A27,'Defensa'!$E$6:$E$10,"Ambos")</f>
+        <f>COUNTIFS('S1'!$B$6:$B$32,$A27,'S1'!$E$6:$E$32,"Diego")+COUNTIFS('S1'!$B$6:$B$32,$A27,'S1'!$E$6:$E$32,"Ambos")+COUNTIFS('S2'!$B$6:$B$23,$A27,'S2'!$E$6:$E$23,"Diego")+COUNTIFS('S2'!$B$6:$B$23,$A27,'S2'!$E$6:$E$23,"Ambos")+COUNTIFS('S3'!$B$6:$B$24,$A27,'S3'!$E$6:$E$24,"Diego")+COUNTIFS('S3'!$B$6:$B$24,$A27,'S3'!$E$6:$E$24,"Ambos")+COUNTIFS('S4'!$B$6:$B$22,$A27,'S4'!$E$6:$E$22,"Diego")+COUNTIFS('S4'!$B$6:$B$22,$A27,'S4'!$E$6:$E$22,"Ambos")+COUNTIFS('S5'!$B$6:$B$20,$A27,'S5'!$E$6:$E$20,"Diego")+COUNTIFS('S5'!$B$6:$B$20,$A27,'S5'!$E$6:$E$20,"Ambos")+COUNTIFS('S6'!$B$6:$B$17,$A27,'S6'!$E$6:$E$17,"Diego")+COUNTIFS('S6'!$B$6:$B$17,$A27,'S6'!$E$6:$E$17,"Ambos")+COUNTIFS('S7'!$B$6:$B$19,$A27,'S7'!$E$6:$E$19,"Diego")+COUNTIFS('S7'!$B$6:$B$19,$A27,'S7'!$E$6:$E$19,"Ambos")+COUNTIFS('S8'!$B$6:$B$23,$A27,'S8'!$E$6:$E$23,"Diego")+COUNTIFS('S8'!$B$6:$B$23,$A27,'S8'!$E$6:$E$23,"Ambos")+COUNTIFS('S9'!$B$6:$B$15,$A27,'S9'!$E$6:$E$15,"Diego")+COUNTIFS('S9'!$B$6:$B$15,$A27,'S9'!$E$6:$E$15,"Ambos")+COUNTIFS('S10'!$B$6:$B$13,$A27,'S10'!$E$6:$E$13,"Diego")+COUNTIFS('S10'!$B$6:$B$13,$A27,'S10'!$E$6:$E$13,"Ambos")+COUNTIFS('Holgura'!$B$6:$B$11,$A27,'Holgura'!$E$6:$E$11,"Diego")+COUNTIFS('Holgura'!$B$6:$B$11,$A27,'Holgura'!$E$6:$E$11,"Ambos")+COUNTIFS('Entrega'!$B$6:$B$9,$A27,'Entrega'!$E$6:$E$9,"Diego")+COUNTIFS('Entrega'!$B$6:$B$9,$A27,'Entrega'!$E$6:$E$9,"Ambos")+COUNTIFS('Defensa'!$B$6:$B$10,$A27,'Defensa'!$E$6:$E$10,"Diego")+COUNTIFS('Defensa'!$B$6:$B$10,$A27,'Defensa'!$E$6:$E$10,"Ambos")</f>
         <v/>
       </c>
     </row>
@@ -9347,19 +9368,19 @@
         <v/>
       </c>
       <c r="D28" s="21">
-        <f>SUMIFS('S1'!$I$6:$I$32,'S1'!$B$6:$B$32,$A28,'S1'!$E$6:$E$32,"Víctor")+SUMIFS('S1'!$I$6:$I$32,'S1'!$B$6:$B$32,$A28,'S1'!$E$6:$E$32,"Ambos")+SUMIFS('S2'!$I$6:$I$23,'S2'!$B$6:$B$23,$A28,'S2'!$E$6:$E$23,"Víctor")+SUMIFS('S2'!$I$6:$I$23,'S2'!$B$6:$B$23,$A28,'S2'!$E$6:$E$23,"Ambos")+SUMIFS('S3'!$I$6:$I$19,'S3'!$B$6:$B$19,$A28,'S3'!$E$6:$E$19,"Víctor")+SUMIFS('S3'!$I$6:$I$19,'S3'!$B$6:$B$19,$A28,'S3'!$E$6:$E$19,"Ambos")+SUMIFS('S4'!$I$6:$I$20,'S4'!$B$6:$B$20,$A28,'S4'!$E$6:$E$20,"Víctor")+SUMIFS('S4'!$I$6:$I$20,'S4'!$B$6:$B$20,$A28,'S4'!$E$6:$E$20,"Ambos")+SUMIFS('S5'!$I$6:$I$20,'S5'!$B$6:$B$20,$A28,'S5'!$E$6:$E$20,"Víctor")+SUMIFS('S5'!$I$6:$I$20,'S5'!$B$6:$B$20,$A28,'S5'!$E$6:$E$20,"Ambos")+SUMIFS('S6'!$I$6:$I$17,'S6'!$B$6:$B$17,$A28,'S6'!$E$6:$E$17,"Víctor")+SUMIFS('S6'!$I$6:$I$17,'S6'!$B$6:$B$17,$A28,'S6'!$E$6:$E$17,"Ambos")+SUMIFS('S7'!$I$6:$I$19,'S7'!$B$6:$B$19,$A28,'S7'!$E$6:$E$19,"Víctor")+SUMIFS('S7'!$I$6:$I$19,'S7'!$B$6:$B$19,$A28,'S7'!$E$6:$E$19,"Ambos")+SUMIFS('S8'!$I$6:$I$23,'S8'!$B$6:$B$23,$A28,'S8'!$E$6:$E$23,"Víctor")+SUMIFS('S8'!$I$6:$I$23,'S8'!$B$6:$B$23,$A28,'S8'!$E$6:$E$23,"Ambos")+SUMIFS('S9'!$I$6:$I$15,'S9'!$B$6:$B$15,$A28,'S9'!$E$6:$E$15,"Víctor")+SUMIFS('S9'!$I$6:$I$15,'S9'!$B$6:$B$15,$A28,'S9'!$E$6:$E$15,"Ambos")+SUMIFS('S10'!$I$6:$I$13,'S10'!$B$6:$B$13,$A28,'S10'!$E$6:$E$13,"Víctor")+SUMIFS('S10'!$I$6:$I$13,'S10'!$B$6:$B$13,$A28,'S10'!$E$6:$E$13,"Ambos")+SUMIFS('Holgura'!$I$6:$I$11,'Holgura'!$B$6:$B$11,$A28,'Holgura'!$E$6:$E$11,"Víctor")+SUMIFS('Holgura'!$I$6:$I$11,'Holgura'!$B$6:$B$11,$A28,'Holgura'!$E$6:$E$11,"Ambos")+SUMIFS('Entrega'!$I$6:$I$9,'Entrega'!$B$6:$B$9,$A28,'Entrega'!$E$6:$E$9,"Víctor")+SUMIFS('Entrega'!$I$6:$I$9,'Entrega'!$B$6:$B$9,$A28,'Entrega'!$E$6:$E$9,"Ambos")+SUMIFS('Defensa'!$I$6:$I$10,'Defensa'!$B$6:$B$10,$A28,'Defensa'!$E$6:$E$10,"Víctor")+SUMIFS('Defensa'!$I$6:$I$10,'Defensa'!$B$6:$B$10,$A28,'Defensa'!$E$6:$E$10,"Ambos")</f>
+        <f>SUMIFS('S1'!$I$6:$I$32,'S1'!$B$6:$B$32,$A28,'S1'!$E$6:$E$32,"Víctor")+SUMIFS('S1'!$I$6:$I$32,'S1'!$B$6:$B$32,$A28,'S1'!$E$6:$E$32,"Ambos")+SUMIFS('S2'!$I$6:$I$23,'S2'!$B$6:$B$23,$A28,'S2'!$E$6:$E$23,"Víctor")+SUMIFS('S2'!$I$6:$I$23,'S2'!$B$6:$B$23,$A28,'S2'!$E$6:$E$23,"Ambos")+SUMIFS('S3'!$I$6:$I$24,'S3'!$B$6:$B$24,$A28,'S3'!$E$6:$E$24,"Víctor")+SUMIFS('S3'!$I$6:$I$24,'S3'!$B$6:$B$24,$A28,'S3'!$E$6:$E$24,"Ambos")+SUMIFS('S4'!$I$6:$I$22,'S4'!$B$6:$B$22,$A28,'S4'!$E$6:$E$22,"Víctor")+SUMIFS('S4'!$I$6:$I$22,'S4'!$B$6:$B$22,$A28,'S4'!$E$6:$E$22,"Ambos")+SUMIFS('S5'!$I$6:$I$20,'S5'!$B$6:$B$20,$A28,'S5'!$E$6:$E$20,"Víctor")+SUMIFS('S5'!$I$6:$I$20,'S5'!$B$6:$B$20,$A28,'S5'!$E$6:$E$20,"Ambos")+SUMIFS('S6'!$I$6:$I$17,'S6'!$B$6:$B$17,$A28,'S6'!$E$6:$E$17,"Víctor")+SUMIFS('S6'!$I$6:$I$17,'S6'!$B$6:$B$17,$A28,'S6'!$E$6:$E$17,"Ambos")+SUMIFS('S7'!$I$6:$I$19,'S7'!$B$6:$B$19,$A28,'S7'!$E$6:$E$19,"Víctor")+SUMIFS('S7'!$I$6:$I$19,'S7'!$B$6:$B$19,$A28,'S7'!$E$6:$E$19,"Ambos")+SUMIFS('S8'!$I$6:$I$23,'S8'!$B$6:$B$23,$A28,'S8'!$E$6:$E$23,"Víctor")+SUMIFS('S8'!$I$6:$I$23,'S8'!$B$6:$B$23,$A28,'S8'!$E$6:$E$23,"Ambos")+SUMIFS('S9'!$I$6:$I$15,'S9'!$B$6:$B$15,$A28,'S9'!$E$6:$E$15,"Víctor")+SUMIFS('S9'!$I$6:$I$15,'S9'!$B$6:$B$15,$A28,'S9'!$E$6:$E$15,"Ambos")+SUMIFS('S10'!$I$6:$I$13,'S10'!$B$6:$B$13,$A28,'S10'!$E$6:$E$13,"Víctor")+SUMIFS('S10'!$I$6:$I$13,'S10'!$B$6:$B$13,$A28,'S10'!$E$6:$E$13,"Ambos")+SUMIFS('Holgura'!$I$6:$I$11,'Holgura'!$B$6:$B$11,$A28,'Holgura'!$E$6:$E$11,"Víctor")+SUMIFS('Holgura'!$I$6:$I$11,'Holgura'!$B$6:$B$11,$A28,'Holgura'!$E$6:$E$11,"Ambos")+SUMIFS('Entrega'!$I$6:$I$9,'Entrega'!$B$6:$B$9,$A28,'Entrega'!$E$6:$E$9,"Víctor")+SUMIFS('Entrega'!$I$6:$I$9,'Entrega'!$B$6:$B$9,$A28,'Entrega'!$E$6:$E$9,"Ambos")+SUMIFS('Defensa'!$I$6:$I$10,'Defensa'!$B$6:$B$10,$A28,'Defensa'!$E$6:$E$10,"Víctor")+SUMIFS('Defensa'!$I$6:$I$10,'Defensa'!$B$6:$B$10,$A28,'Defensa'!$E$6:$E$10,"Ambos")</f>
         <v/>
       </c>
       <c r="E28" s="21">
-        <f>SUMIFS('S1'!$I$6:$I$32,'S1'!$B$6:$B$32,$A28,'S1'!$E$6:$E$32,"Diego")+SUMIFS('S1'!$I$6:$I$32,'S1'!$B$6:$B$32,$A28,'S1'!$E$6:$E$32,"Ambos")+SUMIFS('S2'!$I$6:$I$23,'S2'!$B$6:$B$23,$A28,'S2'!$E$6:$E$23,"Diego")+SUMIFS('S2'!$I$6:$I$23,'S2'!$B$6:$B$23,$A28,'S2'!$E$6:$E$23,"Ambos")+SUMIFS('S3'!$I$6:$I$19,'S3'!$B$6:$B$19,$A28,'S3'!$E$6:$E$19,"Diego")+SUMIFS('S3'!$I$6:$I$19,'S3'!$B$6:$B$19,$A28,'S3'!$E$6:$E$19,"Ambos")+SUMIFS('S4'!$I$6:$I$20,'S4'!$B$6:$B$20,$A28,'S4'!$E$6:$E$20,"Diego")+SUMIFS('S4'!$I$6:$I$20,'S4'!$B$6:$B$20,$A28,'S4'!$E$6:$E$20,"Ambos")+SUMIFS('S5'!$I$6:$I$20,'S5'!$B$6:$B$20,$A28,'S5'!$E$6:$E$20,"Diego")+SUMIFS('S5'!$I$6:$I$20,'S5'!$B$6:$B$20,$A28,'S5'!$E$6:$E$20,"Ambos")+SUMIFS('S6'!$I$6:$I$17,'S6'!$B$6:$B$17,$A28,'S6'!$E$6:$E$17,"Diego")+SUMIFS('S6'!$I$6:$I$17,'S6'!$B$6:$B$17,$A28,'S6'!$E$6:$E$17,"Ambos")+SUMIFS('S7'!$I$6:$I$19,'S7'!$B$6:$B$19,$A28,'S7'!$E$6:$E$19,"Diego")+SUMIFS('S7'!$I$6:$I$19,'S7'!$B$6:$B$19,$A28,'S7'!$E$6:$E$19,"Ambos")+SUMIFS('S8'!$I$6:$I$23,'S8'!$B$6:$B$23,$A28,'S8'!$E$6:$E$23,"Diego")+SUMIFS('S8'!$I$6:$I$23,'S8'!$B$6:$B$23,$A28,'S8'!$E$6:$E$23,"Ambos")+SUMIFS('S9'!$I$6:$I$15,'S9'!$B$6:$B$15,$A28,'S9'!$E$6:$E$15,"Diego")+SUMIFS('S9'!$I$6:$I$15,'S9'!$B$6:$B$15,$A28,'S9'!$E$6:$E$15,"Ambos")+SUMIFS('S10'!$I$6:$I$13,'S10'!$B$6:$B$13,$A28,'S10'!$E$6:$E$13,"Diego")+SUMIFS('S10'!$I$6:$I$13,'S10'!$B$6:$B$13,$A28,'S10'!$E$6:$E$13,"Ambos")+SUMIFS('Holgura'!$I$6:$I$11,'Holgura'!$B$6:$B$11,$A28,'Holgura'!$E$6:$E$11,"Diego")+SUMIFS('Holgura'!$I$6:$I$11,'Holgura'!$B$6:$B$11,$A28,'Holgura'!$E$6:$E$11,"Ambos")+SUMIFS('Entrega'!$I$6:$I$9,'Entrega'!$B$6:$B$9,$A28,'Entrega'!$E$6:$E$9,"Diego")+SUMIFS('Entrega'!$I$6:$I$9,'Entrega'!$B$6:$B$9,$A28,'Entrega'!$E$6:$E$9,"Ambos")+SUMIFS('Defensa'!$I$6:$I$10,'Defensa'!$B$6:$B$10,$A28,'Defensa'!$E$6:$E$10,"Diego")+SUMIFS('Defensa'!$I$6:$I$10,'Defensa'!$B$6:$B$10,$A28,'Defensa'!$E$6:$E$10,"Ambos")</f>
+        <f>SUMIFS('S1'!$I$6:$I$32,'S1'!$B$6:$B$32,$A28,'S1'!$E$6:$E$32,"Diego")+SUMIFS('S1'!$I$6:$I$32,'S1'!$B$6:$B$32,$A28,'S1'!$E$6:$E$32,"Ambos")+SUMIFS('S2'!$I$6:$I$23,'S2'!$B$6:$B$23,$A28,'S2'!$E$6:$E$23,"Diego")+SUMIFS('S2'!$I$6:$I$23,'S2'!$B$6:$B$23,$A28,'S2'!$E$6:$E$23,"Ambos")+SUMIFS('S3'!$I$6:$I$24,'S3'!$B$6:$B$24,$A28,'S3'!$E$6:$E$24,"Diego")+SUMIFS('S3'!$I$6:$I$24,'S3'!$B$6:$B$24,$A28,'S3'!$E$6:$E$24,"Ambos")+SUMIFS('S4'!$I$6:$I$22,'S4'!$B$6:$B$22,$A28,'S4'!$E$6:$E$22,"Diego")+SUMIFS('S4'!$I$6:$I$22,'S4'!$B$6:$B$22,$A28,'S4'!$E$6:$E$22,"Ambos")+SUMIFS('S5'!$I$6:$I$20,'S5'!$B$6:$B$20,$A28,'S5'!$E$6:$E$20,"Diego")+SUMIFS('S5'!$I$6:$I$20,'S5'!$B$6:$B$20,$A28,'S5'!$E$6:$E$20,"Ambos")+SUMIFS('S6'!$I$6:$I$17,'S6'!$B$6:$B$17,$A28,'S6'!$E$6:$E$17,"Diego")+SUMIFS('S6'!$I$6:$I$17,'S6'!$B$6:$B$17,$A28,'S6'!$E$6:$E$17,"Ambos")+SUMIFS('S7'!$I$6:$I$19,'S7'!$B$6:$B$19,$A28,'S7'!$E$6:$E$19,"Diego")+SUMIFS('S7'!$I$6:$I$19,'S7'!$B$6:$B$19,$A28,'S7'!$E$6:$E$19,"Ambos")+SUMIFS('S8'!$I$6:$I$23,'S8'!$B$6:$B$23,$A28,'S8'!$E$6:$E$23,"Diego")+SUMIFS('S8'!$I$6:$I$23,'S8'!$B$6:$B$23,$A28,'S8'!$E$6:$E$23,"Ambos")+SUMIFS('S9'!$I$6:$I$15,'S9'!$B$6:$B$15,$A28,'S9'!$E$6:$E$15,"Diego")+SUMIFS('S9'!$I$6:$I$15,'S9'!$B$6:$B$15,$A28,'S9'!$E$6:$E$15,"Ambos")+SUMIFS('S10'!$I$6:$I$13,'S10'!$B$6:$B$13,$A28,'S10'!$E$6:$E$13,"Diego")+SUMIFS('S10'!$I$6:$I$13,'S10'!$B$6:$B$13,$A28,'S10'!$E$6:$E$13,"Ambos")+SUMIFS('Holgura'!$I$6:$I$11,'Holgura'!$B$6:$B$11,$A28,'Holgura'!$E$6:$E$11,"Diego")+SUMIFS('Holgura'!$I$6:$I$11,'Holgura'!$B$6:$B$11,$A28,'Holgura'!$E$6:$E$11,"Ambos")+SUMIFS('Entrega'!$I$6:$I$9,'Entrega'!$B$6:$B$9,$A28,'Entrega'!$E$6:$E$9,"Diego")+SUMIFS('Entrega'!$I$6:$I$9,'Entrega'!$B$6:$B$9,$A28,'Entrega'!$E$6:$E$9,"Ambos")+SUMIFS('Defensa'!$I$6:$I$10,'Defensa'!$B$6:$B$10,$A28,'Defensa'!$E$6:$E$10,"Diego")+SUMIFS('Defensa'!$I$6:$I$10,'Defensa'!$B$6:$B$10,$A28,'Defensa'!$E$6:$E$10,"Ambos")</f>
         <v/>
       </c>
       <c r="F28" s="21">
-        <f>COUNTIFS('S1'!$B$6:$B$32,$A28,'S1'!$E$6:$E$32,"Víctor")+COUNTIFS('S1'!$B$6:$B$32,$A28,'S1'!$E$6:$E$32,"Ambos")+COUNTIFS('S2'!$B$6:$B$23,$A28,'S2'!$E$6:$E$23,"Víctor")+COUNTIFS('S2'!$B$6:$B$23,$A28,'S2'!$E$6:$E$23,"Ambos")+COUNTIFS('S3'!$B$6:$B$19,$A28,'S3'!$E$6:$E$19,"Víctor")+COUNTIFS('S3'!$B$6:$B$19,$A28,'S3'!$E$6:$E$19,"Ambos")+COUNTIFS('S4'!$B$6:$B$20,$A28,'S4'!$E$6:$E$20,"Víctor")+COUNTIFS('S4'!$B$6:$B$20,$A28,'S4'!$E$6:$E$20,"Ambos")+COUNTIFS('S5'!$B$6:$B$20,$A28,'S5'!$E$6:$E$20,"Víctor")+COUNTIFS('S5'!$B$6:$B$20,$A28,'S5'!$E$6:$E$20,"Ambos")+COUNTIFS('S6'!$B$6:$B$17,$A28,'S6'!$E$6:$E$17,"Víctor")+COUNTIFS('S6'!$B$6:$B$17,$A28,'S6'!$E$6:$E$17,"Ambos")+COUNTIFS('S7'!$B$6:$B$19,$A28,'S7'!$E$6:$E$19,"Víctor")+COUNTIFS('S7'!$B$6:$B$19,$A28,'S7'!$E$6:$E$19,"Ambos")+COUNTIFS('S8'!$B$6:$B$23,$A28,'S8'!$E$6:$E$23,"Víctor")+COUNTIFS('S8'!$B$6:$B$23,$A28,'S8'!$E$6:$E$23,"Ambos")+COUNTIFS('S9'!$B$6:$B$15,$A28,'S9'!$E$6:$E$15,"Víctor")+COUNTIFS('S9'!$B$6:$B$15,$A28,'S9'!$E$6:$E$15,"Ambos")+COUNTIFS('S10'!$B$6:$B$13,$A28,'S10'!$E$6:$E$13,"Víctor")+COUNTIFS('S10'!$B$6:$B$13,$A28,'S10'!$E$6:$E$13,"Ambos")+COUNTIFS('Holgura'!$B$6:$B$11,$A28,'Holgura'!$E$6:$E$11,"Víctor")+COUNTIFS('Holgura'!$B$6:$B$11,$A28,'Holgura'!$E$6:$E$11,"Ambos")+COUNTIFS('Entrega'!$B$6:$B$9,$A28,'Entrega'!$E$6:$E$9,"Víctor")+COUNTIFS('Entrega'!$B$6:$B$9,$A28,'Entrega'!$E$6:$E$9,"Ambos")+COUNTIFS('Defensa'!$B$6:$B$10,$A28,'Defensa'!$E$6:$E$10,"Víctor")+COUNTIFS('Defensa'!$B$6:$B$10,$A28,'Defensa'!$E$6:$E$10,"Ambos")</f>
+        <f>COUNTIFS('S1'!$B$6:$B$32,$A28,'S1'!$E$6:$E$32,"Víctor")+COUNTIFS('S1'!$B$6:$B$32,$A28,'S1'!$E$6:$E$32,"Ambos")+COUNTIFS('S2'!$B$6:$B$23,$A28,'S2'!$E$6:$E$23,"Víctor")+COUNTIFS('S2'!$B$6:$B$23,$A28,'S2'!$E$6:$E$23,"Ambos")+COUNTIFS('S3'!$B$6:$B$24,$A28,'S3'!$E$6:$E$24,"Víctor")+COUNTIFS('S3'!$B$6:$B$24,$A28,'S3'!$E$6:$E$24,"Ambos")+COUNTIFS('S4'!$B$6:$B$22,$A28,'S4'!$E$6:$E$22,"Víctor")+COUNTIFS('S4'!$B$6:$B$22,$A28,'S4'!$E$6:$E$22,"Ambos")+COUNTIFS('S5'!$B$6:$B$20,$A28,'S5'!$E$6:$E$20,"Víctor")+COUNTIFS('S5'!$B$6:$B$20,$A28,'S5'!$E$6:$E$20,"Ambos")+COUNTIFS('S6'!$B$6:$B$17,$A28,'S6'!$E$6:$E$17,"Víctor")+COUNTIFS('S6'!$B$6:$B$17,$A28,'S6'!$E$6:$E$17,"Ambos")+COUNTIFS('S7'!$B$6:$B$19,$A28,'S7'!$E$6:$E$19,"Víctor")+COUNTIFS('S7'!$B$6:$B$19,$A28,'S7'!$E$6:$E$19,"Ambos")+COUNTIFS('S8'!$B$6:$B$23,$A28,'S8'!$E$6:$E$23,"Víctor")+COUNTIFS('S8'!$B$6:$B$23,$A28,'S8'!$E$6:$E$23,"Ambos")+COUNTIFS('S9'!$B$6:$B$15,$A28,'S9'!$E$6:$E$15,"Víctor")+COUNTIFS('S9'!$B$6:$B$15,$A28,'S9'!$E$6:$E$15,"Ambos")+COUNTIFS('S10'!$B$6:$B$13,$A28,'S10'!$E$6:$E$13,"Víctor")+COUNTIFS('S10'!$B$6:$B$13,$A28,'S10'!$E$6:$E$13,"Ambos")+COUNTIFS('Holgura'!$B$6:$B$11,$A28,'Holgura'!$E$6:$E$11,"Víctor")+COUNTIFS('Holgura'!$B$6:$B$11,$A28,'Holgura'!$E$6:$E$11,"Ambos")+COUNTIFS('Entrega'!$B$6:$B$9,$A28,'Entrega'!$E$6:$E$9,"Víctor")+COUNTIFS('Entrega'!$B$6:$B$9,$A28,'Entrega'!$E$6:$E$9,"Ambos")+COUNTIFS('Defensa'!$B$6:$B$10,$A28,'Defensa'!$E$6:$E$10,"Víctor")+COUNTIFS('Defensa'!$B$6:$B$10,$A28,'Defensa'!$E$6:$E$10,"Ambos")</f>
         <v/>
       </c>
       <c r="G28" s="21">
-        <f>COUNTIFS('S1'!$B$6:$B$32,$A28,'S1'!$E$6:$E$32,"Diego")+COUNTIFS('S1'!$B$6:$B$32,$A28,'S1'!$E$6:$E$32,"Ambos")+COUNTIFS('S2'!$B$6:$B$23,$A28,'S2'!$E$6:$E$23,"Diego")+COUNTIFS('S2'!$B$6:$B$23,$A28,'S2'!$E$6:$E$23,"Ambos")+COUNTIFS('S3'!$B$6:$B$19,$A28,'S3'!$E$6:$E$19,"Diego")+COUNTIFS('S3'!$B$6:$B$19,$A28,'S3'!$E$6:$E$19,"Ambos")+COUNTIFS('S4'!$B$6:$B$20,$A28,'S4'!$E$6:$E$20,"Diego")+COUNTIFS('S4'!$B$6:$B$20,$A28,'S4'!$E$6:$E$20,"Ambos")+COUNTIFS('S5'!$B$6:$B$20,$A28,'S5'!$E$6:$E$20,"Diego")+COUNTIFS('S5'!$B$6:$B$20,$A28,'S5'!$E$6:$E$20,"Ambos")+COUNTIFS('S6'!$B$6:$B$17,$A28,'S6'!$E$6:$E$17,"Diego")+COUNTIFS('S6'!$B$6:$B$17,$A28,'S6'!$E$6:$E$17,"Ambos")+COUNTIFS('S7'!$B$6:$B$19,$A28,'S7'!$E$6:$E$19,"Diego")+COUNTIFS('S7'!$B$6:$B$19,$A28,'S7'!$E$6:$E$19,"Ambos")+COUNTIFS('S8'!$B$6:$B$23,$A28,'S8'!$E$6:$E$23,"Diego")+COUNTIFS('S8'!$B$6:$B$23,$A28,'S8'!$E$6:$E$23,"Ambos")+COUNTIFS('S9'!$B$6:$B$15,$A28,'S9'!$E$6:$E$15,"Diego")+COUNTIFS('S9'!$B$6:$B$15,$A28,'S9'!$E$6:$E$15,"Ambos")+COUNTIFS('S10'!$B$6:$B$13,$A28,'S10'!$E$6:$E$13,"Diego")+COUNTIFS('S10'!$B$6:$B$13,$A28,'S10'!$E$6:$E$13,"Ambos")+COUNTIFS('Holgura'!$B$6:$B$11,$A28,'Holgura'!$E$6:$E$11,"Diego")+COUNTIFS('Holgura'!$B$6:$B$11,$A28,'Holgura'!$E$6:$E$11,"Ambos")+COUNTIFS('Entrega'!$B$6:$B$9,$A28,'Entrega'!$E$6:$E$9,"Diego")+COUNTIFS('Entrega'!$B$6:$B$9,$A28,'Entrega'!$E$6:$E$9,"Ambos")+COUNTIFS('Defensa'!$B$6:$B$10,$A28,'Defensa'!$E$6:$E$10,"Diego")+COUNTIFS('Defensa'!$B$6:$B$10,$A28,'Defensa'!$E$6:$E$10,"Ambos")</f>
+        <f>COUNTIFS('S1'!$B$6:$B$32,$A28,'S1'!$E$6:$E$32,"Diego")+COUNTIFS('S1'!$B$6:$B$32,$A28,'S1'!$E$6:$E$32,"Ambos")+COUNTIFS('S2'!$B$6:$B$23,$A28,'S2'!$E$6:$E$23,"Diego")+COUNTIFS('S2'!$B$6:$B$23,$A28,'S2'!$E$6:$E$23,"Ambos")+COUNTIFS('S3'!$B$6:$B$24,$A28,'S3'!$E$6:$E$24,"Diego")+COUNTIFS('S3'!$B$6:$B$24,$A28,'S3'!$E$6:$E$24,"Ambos")+COUNTIFS('S4'!$B$6:$B$22,$A28,'S4'!$E$6:$E$22,"Diego")+COUNTIFS('S4'!$B$6:$B$22,$A28,'S4'!$E$6:$E$22,"Ambos")+COUNTIFS('S5'!$B$6:$B$20,$A28,'S5'!$E$6:$E$20,"Diego")+COUNTIFS('S5'!$B$6:$B$20,$A28,'S5'!$E$6:$E$20,"Ambos")+COUNTIFS('S6'!$B$6:$B$17,$A28,'S6'!$E$6:$E$17,"Diego")+COUNTIFS('S6'!$B$6:$B$17,$A28,'S6'!$E$6:$E$17,"Ambos")+COUNTIFS('S7'!$B$6:$B$19,$A28,'S7'!$E$6:$E$19,"Diego")+COUNTIFS('S7'!$B$6:$B$19,$A28,'S7'!$E$6:$E$19,"Ambos")+COUNTIFS('S8'!$B$6:$B$23,$A28,'S8'!$E$6:$E$23,"Diego")+COUNTIFS('S8'!$B$6:$B$23,$A28,'S8'!$E$6:$E$23,"Ambos")+COUNTIFS('S9'!$B$6:$B$15,$A28,'S9'!$E$6:$E$15,"Diego")+COUNTIFS('S9'!$B$6:$B$15,$A28,'S9'!$E$6:$E$15,"Ambos")+COUNTIFS('S10'!$B$6:$B$13,$A28,'S10'!$E$6:$E$13,"Diego")+COUNTIFS('S10'!$B$6:$B$13,$A28,'S10'!$E$6:$E$13,"Ambos")+COUNTIFS('Holgura'!$B$6:$B$11,$A28,'Holgura'!$E$6:$E$11,"Diego")+COUNTIFS('Holgura'!$B$6:$B$11,$A28,'Holgura'!$E$6:$E$11,"Ambos")+COUNTIFS('Entrega'!$B$6:$B$9,$A28,'Entrega'!$E$6:$E$9,"Diego")+COUNTIFS('Entrega'!$B$6:$B$9,$A28,'Entrega'!$E$6:$E$9,"Ambos")+COUNTIFS('Defensa'!$B$6:$B$10,$A28,'Defensa'!$E$6:$E$10,"Diego")+COUNTIFS('Defensa'!$B$6:$B$10,$A28,'Defensa'!$E$6:$E$10,"Ambos")</f>
         <v/>
       </c>
     </row>
@@ -9376,19 +9397,19 @@
         <v/>
       </c>
       <c r="D29" s="21">
-        <f>SUMIFS('S1'!$I$6:$I$32,'S1'!$B$6:$B$32,$A29,'S1'!$E$6:$E$32,"Víctor")+SUMIFS('S1'!$I$6:$I$32,'S1'!$B$6:$B$32,$A29,'S1'!$E$6:$E$32,"Ambos")+SUMIFS('S2'!$I$6:$I$23,'S2'!$B$6:$B$23,$A29,'S2'!$E$6:$E$23,"Víctor")+SUMIFS('S2'!$I$6:$I$23,'S2'!$B$6:$B$23,$A29,'S2'!$E$6:$E$23,"Ambos")+SUMIFS('S3'!$I$6:$I$19,'S3'!$B$6:$B$19,$A29,'S3'!$E$6:$E$19,"Víctor")+SUMIFS('S3'!$I$6:$I$19,'S3'!$B$6:$B$19,$A29,'S3'!$E$6:$E$19,"Ambos")+SUMIFS('S4'!$I$6:$I$20,'S4'!$B$6:$B$20,$A29,'S4'!$E$6:$E$20,"Víctor")+SUMIFS('S4'!$I$6:$I$20,'S4'!$B$6:$B$20,$A29,'S4'!$E$6:$E$20,"Ambos")+SUMIFS('S5'!$I$6:$I$20,'S5'!$B$6:$B$20,$A29,'S5'!$E$6:$E$20,"Víctor")+SUMIFS('S5'!$I$6:$I$20,'S5'!$B$6:$B$20,$A29,'S5'!$E$6:$E$20,"Ambos")+SUMIFS('S6'!$I$6:$I$17,'S6'!$B$6:$B$17,$A29,'S6'!$E$6:$E$17,"Víctor")+SUMIFS('S6'!$I$6:$I$17,'S6'!$B$6:$B$17,$A29,'S6'!$E$6:$E$17,"Ambos")+SUMIFS('S7'!$I$6:$I$19,'S7'!$B$6:$B$19,$A29,'S7'!$E$6:$E$19,"Víctor")+SUMIFS('S7'!$I$6:$I$19,'S7'!$B$6:$B$19,$A29,'S7'!$E$6:$E$19,"Ambos")+SUMIFS('S8'!$I$6:$I$23,'S8'!$B$6:$B$23,$A29,'S8'!$E$6:$E$23,"Víctor")+SUMIFS('S8'!$I$6:$I$23,'S8'!$B$6:$B$23,$A29,'S8'!$E$6:$E$23,"Ambos")+SUMIFS('S9'!$I$6:$I$15,'S9'!$B$6:$B$15,$A29,'S9'!$E$6:$E$15,"Víctor")+SUMIFS('S9'!$I$6:$I$15,'S9'!$B$6:$B$15,$A29,'S9'!$E$6:$E$15,"Ambos")+SUMIFS('S10'!$I$6:$I$13,'S10'!$B$6:$B$13,$A29,'S10'!$E$6:$E$13,"Víctor")+SUMIFS('S10'!$I$6:$I$13,'S10'!$B$6:$B$13,$A29,'S10'!$E$6:$E$13,"Ambos")+SUMIFS('Holgura'!$I$6:$I$11,'Holgura'!$B$6:$B$11,$A29,'Holgura'!$E$6:$E$11,"Víctor")+SUMIFS('Holgura'!$I$6:$I$11,'Holgura'!$B$6:$B$11,$A29,'Holgura'!$E$6:$E$11,"Ambos")+SUMIFS('Entrega'!$I$6:$I$9,'Entrega'!$B$6:$B$9,$A29,'Entrega'!$E$6:$E$9,"Víctor")+SUMIFS('Entrega'!$I$6:$I$9,'Entrega'!$B$6:$B$9,$A29,'Entrega'!$E$6:$E$9,"Ambos")+SUMIFS('Defensa'!$I$6:$I$10,'Defensa'!$B$6:$B$10,$A29,'Defensa'!$E$6:$E$10,"Víctor")+SUMIFS('Defensa'!$I$6:$I$10,'Defensa'!$B$6:$B$10,$A29,'Defensa'!$E$6:$E$10,"Ambos")</f>
+        <f>SUMIFS('S1'!$I$6:$I$32,'S1'!$B$6:$B$32,$A29,'S1'!$E$6:$E$32,"Víctor")+SUMIFS('S1'!$I$6:$I$32,'S1'!$B$6:$B$32,$A29,'S1'!$E$6:$E$32,"Ambos")+SUMIFS('S2'!$I$6:$I$23,'S2'!$B$6:$B$23,$A29,'S2'!$E$6:$E$23,"Víctor")+SUMIFS('S2'!$I$6:$I$23,'S2'!$B$6:$B$23,$A29,'S2'!$E$6:$E$23,"Ambos")+SUMIFS('S3'!$I$6:$I$24,'S3'!$B$6:$B$24,$A29,'S3'!$E$6:$E$24,"Víctor")+SUMIFS('S3'!$I$6:$I$24,'S3'!$B$6:$B$24,$A29,'S3'!$E$6:$E$24,"Ambos")+SUMIFS('S4'!$I$6:$I$22,'S4'!$B$6:$B$22,$A29,'S4'!$E$6:$E$22,"Víctor")+SUMIFS('S4'!$I$6:$I$22,'S4'!$B$6:$B$22,$A29,'S4'!$E$6:$E$22,"Ambos")+SUMIFS('S5'!$I$6:$I$20,'S5'!$B$6:$B$20,$A29,'S5'!$E$6:$E$20,"Víctor")+SUMIFS('S5'!$I$6:$I$20,'S5'!$B$6:$B$20,$A29,'S5'!$E$6:$E$20,"Ambos")+SUMIFS('S6'!$I$6:$I$17,'S6'!$B$6:$B$17,$A29,'S6'!$E$6:$E$17,"Víctor")+SUMIFS('S6'!$I$6:$I$17,'S6'!$B$6:$B$17,$A29,'S6'!$E$6:$E$17,"Ambos")+SUMIFS('S7'!$I$6:$I$19,'S7'!$B$6:$B$19,$A29,'S7'!$E$6:$E$19,"Víctor")+SUMIFS('S7'!$I$6:$I$19,'S7'!$B$6:$B$19,$A29,'S7'!$E$6:$E$19,"Ambos")+SUMIFS('S8'!$I$6:$I$23,'S8'!$B$6:$B$23,$A29,'S8'!$E$6:$E$23,"Víctor")+SUMIFS('S8'!$I$6:$I$23,'S8'!$B$6:$B$23,$A29,'S8'!$E$6:$E$23,"Ambos")+SUMIFS('S9'!$I$6:$I$15,'S9'!$B$6:$B$15,$A29,'S9'!$E$6:$E$15,"Víctor")+SUMIFS('S9'!$I$6:$I$15,'S9'!$B$6:$B$15,$A29,'S9'!$E$6:$E$15,"Ambos")+SUMIFS('S10'!$I$6:$I$13,'S10'!$B$6:$B$13,$A29,'S10'!$E$6:$E$13,"Víctor")+SUMIFS('S10'!$I$6:$I$13,'S10'!$B$6:$B$13,$A29,'S10'!$E$6:$E$13,"Ambos")+SUMIFS('Holgura'!$I$6:$I$11,'Holgura'!$B$6:$B$11,$A29,'Holgura'!$E$6:$E$11,"Víctor")+SUMIFS('Holgura'!$I$6:$I$11,'Holgura'!$B$6:$B$11,$A29,'Holgura'!$E$6:$E$11,"Ambos")+SUMIFS('Entrega'!$I$6:$I$9,'Entrega'!$B$6:$B$9,$A29,'Entrega'!$E$6:$E$9,"Víctor")+SUMIFS('Entrega'!$I$6:$I$9,'Entrega'!$B$6:$B$9,$A29,'Entrega'!$E$6:$E$9,"Ambos")+SUMIFS('Defensa'!$I$6:$I$10,'Defensa'!$B$6:$B$10,$A29,'Defensa'!$E$6:$E$10,"Víctor")+SUMIFS('Defensa'!$I$6:$I$10,'Defensa'!$B$6:$B$10,$A29,'Defensa'!$E$6:$E$10,"Ambos")</f>
         <v/>
       </c>
       <c r="E29" s="21">
-        <f>SUMIFS('S1'!$I$6:$I$32,'S1'!$B$6:$B$32,$A29,'S1'!$E$6:$E$32,"Diego")+SUMIFS('S1'!$I$6:$I$32,'S1'!$B$6:$B$32,$A29,'S1'!$E$6:$E$32,"Ambos")+SUMIFS('S2'!$I$6:$I$23,'S2'!$B$6:$B$23,$A29,'S2'!$E$6:$E$23,"Diego")+SUMIFS('S2'!$I$6:$I$23,'S2'!$B$6:$B$23,$A29,'S2'!$E$6:$E$23,"Ambos")+SUMIFS('S3'!$I$6:$I$19,'S3'!$B$6:$B$19,$A29,'S3'!$E$6:$E$19,"Diego")+SUMIFS('S3'!$I$6:$I$19,'S3'!$B$6:$B$19,$A29,'S3'!$E$6:$E$19,"Ambos")+SUMIFS('S4'!$I$6:$I$20,'S4'!$B$6:$B$20,$A29,'S4'!$E$6:$E$20,"Diego")+SUMIFS('S4'!$I$6:$I$20,'S4'!$B$6:$B$20,$A29,'S4'!$E$6:$E$20,"Ambos")+SUMIFS('S5'!$I$6:$I$20,'S5'!$B$6:$B$20,$A29,'S5'!$E$6:$E$20,"Diego")+SUMIFS('S5'!$I$6:$I$20,'S5'!$B$6:$B$20,$A29,'S5'!$E$6:$E$20,"Ambos")+SUMIFS('S6'!$I$6:$I$17,'S6'!$B$6:$B$17,$A29,'S6'!$E$6:$E$17,"Diego")+SUMIFS('S6'!$I$6:$I$17,'S6'!$B$6:$B$17,$A29,'S6'!$E$6:$E$17,"Ambos")+SUMIFS('S7'!$I$6:$I$19,'S7'!$B$6:$B$19,$A29,'S7'!$E$6:$E$19,"Diego")+SUMIFS('S7'!$I$6:$I$19,'S7'!$B$6:$B$19,$A29,'S7'!$E$6:$E$19,"Ambos")+SUMIFS('S8'!$I$6:$I$23,'S8'!$B$6:$B$23,$A29,'S8'!$E$6:$E$23,"Diego")+SUMIFS('S8'!$I$6:$I$23,'S8'!$B$6:$B$23,$A29,'S8'!$E$6:$E$23,"Ambos")+SUMIFS('S9'!$I$6:$I$15,'S9'!$B$6:$B$15,$A29,'S9'!$E$6:$E$15,"Diego")+SUMIFS('S9'!$I$6:$I$15,'S9'!$B$6:$B$15,$A29,'S9'!$E$6:$E$15,"Ambos")+SUMIFS('S10'!$I$6:$I$13,'S10'!$B$6:$B$13,$A29,'S10'!$E$6:$E$13,"Diego")+SUMIFS('S10'!$I$6:$I$13,'S10'!$B$6:$B$13,$A29,'S10'!$E$6:$E$13,"Ambos")+SUMIFS('Holgura'!$I$6:$I$11,'Holgura'!$B$6:$B$11,$A29,'Holgura'!$E$6:$E$11,"Diego")+SUMIFS('Holgura'!$I$6:$I$11,'Holgura'!$B$6:$B$11,$A29,'Holgura'!$E$6:$E$11,"Ambos")+SUMIFS('Entrega'!$I$6:$I$9,'Entrega'!$B$6:$B$9,$A29,'Entrega'!$E$6:$E$9,"Diego")+SUMIFS('Entrega'!$I$6:$I$9,'Entrega'!$B$6:$B$9,$A29,'Entrega'!$E$6:$E$9,"Ambos")+SUMIFS('Defensa'!$I$6:$I$10,'Defensa'!$B$6:$B$10,$A29,'Defensa'!$E$6:$E$10,"Diego")+SUMIFS('Defensa'!$I$6:$I$10,'Defensa'!$B$6:$B$10,$A29,'Defensa'!$E$6:$E$10,"Ambos")</f>
+        <f>SUMIFS('S1'!$I$6:$I$32,'S1'!$B$6:$B$32,$A29,'S1'!$E$6:$E$32,"Diego")+SUMIFS('S1'!$I$6:$I$32,'S1'!$B$6:$B$32,$A29,'S1'!$E$6:$E$32,"Ambos")+SUMIFS('S2'!$I$6:$I$23,'S2'!$B$6:$B$23,$A29,'S2'!$E$6:$E$23,"Diego")+SUMIFS('S2'!$I$6:$I$23,'S2'!$B$6:$B$23,$A29,'S2'!$E$6:$E$23,"Ambos")+SUMIFS('S3'!$I$6:$I$24,'S3'!$B$6:$B$24,$A29,'S3'!$E$6:$E$24,"Diego")+SUMIFS('S3'!$I$6:$I$24,'S3'!$B$6:$B$24,$A29,'S3'!$E$6:$E$24,"Ambos")+SUMIFS('S4'!$I$6:$I$22,'S4'!$B$6:$B$22,$A29,'S4'!$E$6:$E$22,"Diego")+SUMIFS('S4'!$I$6:$I$22,'S4'!$B$6:$B$22,$A29,'S4'!$E$6:$E$22,"Ambos")+SUMIFS('S5'!$I$6:$I$20,'S5'!$B$6:$B$20,$A29,'S5'!$E$6:$E$20,"Diego")+SUMIFS('S5'!$I$6:$I$20,'S5'!$B$6:$B$20,$A29,'S5'!$E$6:$E$20,"Ambos")+SUMIFS('S6'!$I$6:$I$17,'S6'!$B$6:$B$17,$A29,'S6'!$E$6:$E$17,"Diego")+SUMIFS('S6'!$I$6:$I$17,'S6'!$B$6:$B$17,$A29,'S6'!$E$6:$E$17,"Ambos")+SUMIFS('S7'!$I$6:$I$19,'S7'!$B$6:$B$19,$A29,'S7'!$E$6:$E$19,"Diego")+SUMIFS('S7'!$I$6:$I$19,'S7'!$B$6:$B$19,$A29,'S7'!$E$6:$E$19,"Ambos")+SUMIFS('S8'!$I$6:$I$23,'S8'!$B$6:$B$23,$A29,'S8'!$E$6:$E$23,"Diego")+SUMIFS('S8'!$I$6:$I$23,'S8'!$B$6:$B$23,$A29,'S8'!$E$6:$E$23,"Ambos")+SUMIFS('S9'!$I$6:$I$15,'S9'!$B$6:$B$15,$A29,'S9'!$E$6:$E$15,"Diego")+SUMIFS('S9'!$I$6:$I$15,'S9'!$B$6:$B$15,$A29,'S9'!$E$6:$E$15,"Ambos")+SUMIFS('S10'!$I$6:$I$13,'S10'!$B$6:$B$13,$A29,'S10'!$E$6:$E$13,"Diego")+SUMIFS('S10'!$I$6:$I$13,'S10'!$B$6:$B$13,$A29,'S10'!$E$6:$E$13,"Ambos")+SUMIFS('Holgura'!$I$6:$I$11,'Holgura'!$B$6:$B$11,$A29,'Holgura'!$E$6:$E$11,"Diego")+SUMIFS('Holgura'!$I$6:$I$11,'Holgura'!$B$6:$B$11,$A29,'Holgura'!$E$6:$E$11,"Ambos")+SUMIFS('Entrega'!$I$6:$I$9,'Entrega'!$B$6:$B$9,$A29,'Entrega'!$E$6:$E$9,"Diego")+SUMIFS('Entrega'!$I$6:$I$9,'Entrega'!$B$6:$B$9,$A29,'Entrega'!$E$6:$E$9,"Ambos")+SUMIFS('Defensa'!$I$6:$I$10,'Defensa'!$B$6:$B$10,$A29,'Defensa'!$E$6:$E$10,"Diego")+SUMIFS('Defensa'!$I$6:$I$10,'Defensa'!$B$6:$B$10,$A29,'Defensa'!$E$6:$E$10,"Ambos")</f>
         <v/>
       </c>
       <c r="F29" s="21">
-        <f>COUNTIFS('S1'!$B$6:$B$32,$A29,'S1'!$E$6:$E$32,"Víctor")+COUNTIFS('S1'!$B$6:$B$32,$A29,'S1'!$E$6:$E$32,"Ambos")+COUNTIFS('S2'!$B$6:$B$23,$A29,'S2'!$E$6:$E$23,"Víctor")+COUNTIFS('S2'!$B$6:$B$23,$A29,'S2'!$E$6:$E$23,"Ambos")+COUNTIFS('S3'!$B$6:$B$19,$A29,'S3'!$E$6:$E$19,"Víctor")+COUNTIFS('S3'!$B$6:$B$19,$A29,'S3'!$E$6:$E$19,"Ambos")+COUNTIFS('S4'!$B$6:$B$20,$A29,'S4'!$E$6:$E$20,"Víctor")+COUNTIFS('S4'!$B$6:$B$20,$A29,'S4'!$E$6:$E$20,"Ambos")+COUNTIFS('S5'!$B$6:$B$20,$A29,'S5'!$E$6:$E$20,"Víctor")+COUNTIFS('S5'!$B$6:$B$20,$A29,'S5'!$E$6:$E$20,"Ambos")+COUNTIFS('S6'!$B$6:$B$17,$A29,'S6'!$E$6:$E$17,"Víctor")+COUNTIFS('S6'!$B$6:$B$17,$A29,'S6'!$E$6:$E$17,"Ambos")+COUNTIFS('S7'!$B$6:$B$19,$A29,'S7'!$E$6:$E$19,"Víctor")+COUNTIFS('S7'!$B$6:$B$19,$A29,'S7'!$E$6:$E$19,"Ambos")+COUNTIFS('S8'!$B$6:$B$23,$A29,'S8'!$E$6:$E$23,"Víctor")+COUNTIFS('S8'!$B$6:$B$23,$A29,'S8'!$E$6:$E$23,"Ambos")+COUNTIFS('S9'!$B$6:$B$15,$A29,'S9'!$E$6:$E$15,"Víctor")+COUNTIFS('S9'!$B$6:$B$15,$A29,'S9'!$E$6:$E$15,"Ambos")+COUNTIFS('S10'!$B$6:$B$13,$A29,'S10'!$E$6:$E$13,"Víctor")+COUNTIFS('S10'!$B$6:$B$13,$A29,'S10'!$E$6:$E$13,"Ambos")+COUNTIFS('Holgura'!$B$6:$B$11,$A29,'Holgura'!$E$6:$E$11,"Víctor")+COUNTIFS('Holgura'!$B$6:$B$11,$A29,'Holgura'!$E$6:$E$11,"Ambos")+COUNTIFS('Entrega'!$B$6:$B$9,$A29,'Entrega'!$E$6:$E$9,"Víctor")+COUNTIFS('Entrega'!$B$6:$B$9,$A29,'Entrega'!$E$6:$E$9,"Ambos")+COUNTIFS('Defensa'!$B$6:$B$10,$A29,'Defensa'!$E$6:$E$10,"Víctor")+COUNTIFS('Defensa'!$B$6:$B$10,$A29,'Defensa'!$E$6:$E$10,"Ambos")</f>
+        <f>COUNTIFS('S1'!$B$6:$B$32,$A29,'S1'!$E$6:$E$32,"Víctor")+COUNTIFS('S1'!$B$6:$B$32,$A29,'S1'!$E$6:$E$32,"Ambos")+COUNTIFS('S2'!$B$6:$B$23,$A29,'S2'!$E$6:$E$23,"Víctor")+COUNTIFS('S2'!$B$6:$B$23,$A29,'S2'!$E$6:$E$23,"Ambos")+COUNTIFS('S3'!$B$6:$B$24,$A29,'S3'!$E$6:$E$24,"Víctor")+COUNTIFS('S3'!$B$6:$B$24,$A29,'S3'!$E$6:$E$24,"Ambos")+COUNTIFS('S4'!$B$6:$B$22,$A29,'S4'!$E$6:$E$22,"Víctor")+COUNTIFS('S4'!$B$6:$B$22,$A29,'S4'!$E$6:$E$22,"Ambos")+COUNTIFS('S5'!$B$6:$B$20,$A29,'S5'!$E$6:$E$20,"Víctor")+COUNTIFS('S5'!$B$6:$B$20,$A29,'S5'!$E$6:$E$20,"Ambos")+COUNTIFS('S6'!$B$6:$B$17,$A29,'S6'!$E$6:$E$17,"Víctor")+COUNTIFS('S6'!$B$6:$B$17,$A29,'S6'!$E$6:$E$17,"Ambos")+COUNTIFS('S7'!$B$6:$B$19,$A29,'S7'!$E$6:$E$19,"Víctor")+COUNTIFS('S7'!$B$6:$B$19,$A29,'S7'!$E$6:$E$19,"Ambos")+COUNTIFS('S8'!$B$6:$B$23,$A29,'S8'!$E$6:$E$23,"Víctor")+COUNTIFS('S8'!$B$6:$B$23,$A29,'S8'!$E$6:$E$23,"Ambos")+COUNTIFS('S9'!$B$6:$B$15,$A29,'S9'!$E$6:$E$15,"Víctor")+COUNTIFS('S9'!$B$6:$B$15,$A29,'S9'!$E$6:$E$15,"Ambos")+COUNTIFS('S10'!$B$6:$B$13,$A29,'S10'!$E$6:$E$13,"Víctor")+COUNTIFS('S10'!$B$6:$B$13,$A29,'S10'!$E$6:$E$13,"Ambos")+COUNTIFS('Holgura'!$B$6:$B$11,$A29,'Holgura'!$E$6:$E$11,"Víctor")+COUNTIFS('Holgura'!$B$6:$B$11,$A29,'Holgura'!$E$6:$E$11,"Ambos")+COUNTIFS('Entrega'!$B$6:$B$9,$A29,'Entrega'!$E$6:$E$9,"Víctor")+COUNTIFS('Entrega'!$B$6:$B$9,$A29,'Entrega'!$E$6:$E$9,"Ambos")+COUNTIFS('Defensa'!$B$6:$B$10,$A29,'Defensa'!$E$6:$E$10,"Víctor")+COUNTIFS('Defensa'!$B$6:$B$10,$A29,'Defensa'!$E$6:$E$10,"Ambos")</f>
         <v/>
       </c>
       <c r="G29" s="21">
-        <f>COUNTIFS('S1'!$B$6:$B$32,$A29,'S1'!$E$6:$E$32,"Diego")+COUNTIFS('S1'!$B$6:$B$32,$A29,'S1'!$E$6:$E$32,"Ambos")+COUNTIFS('S2'!$B$6:$B$23,$A29,'S2'!$E$6:$E$23,"Diego")+COUNTIFS('S2'!$B$6:$B$23,$A29,'S2'!$E$6:$E$23,"Ambos")+COUNTIFS('S3'!$B$6:$B$19,$A29,'S3'!$E$6:$E$19,"Diego")+COUNTIFS('S3'!$B$6:$B$19,$A29,'S3'!$E$6:$E$19,"Ambos")+COUNTIFS('S4'!$B$6:$B$20,$A29,'S4'!$E$6:$E$20,"Diego")+COUNTIFS('S4'!$B$6:$B$20,$A29,'S4'!$E$6:$E$20,"Ambos")+COUNTIFS('S5'!$B$6:$B$20,$A29,'S5'!$E$6:$E$20,"Diego")+COUNTIFS('S5'!$B$6:$B$20,$A29,'S5'!$E$6:$E$20,"Ambos")+COUNTIFS('S6'!$B$6:$B$17,$A29,'S6'!$E$6:$E$17,"Diego")+COUNTIFS('S6'!$B$6:$B$17,$A29,'S6'!$E$6:$E$17,"Ambos")+COUNTIFS('S7'!$B$6:$B$19,$A29,'S7'!$E$6:$E$19,"Diego")+COUNTIFS('S7'!$B$6:$B$19,$A29,'S7'!$E$6:$E$19,"Ambos")+COUNTIFS('S8'!$B$6:$B$23,$A29,'S8'!$E$6:$E$23,"Diego")+COUNTIFS('S8'!$B$6:$B$23,$A29,'S8'!$E$6:$E$23,"Ambos")+COUNTIFS('S9'!$B$6:$B$15,$A29,'S9'!$E$6:$E$15,"Diego")+COUNTIFS('S9'!$B$6:$B$15,$A29,'S9'!$E$6:$E$15,"Ambos")+COUNTIFS('S10'!$B$6:$B$13,$A29,'S10'!$E$6:$E$13,"Diego")+COUNTIFS('S10'!$B$6:$B$13,$A29,'S10'!$E$6:$E$13,"Ambos")+COUNTIFS('Holgura'!$B$6:$B$11,$A29,'Holgura'!$E$6:$E$11,"Diego")+COUNTIFS('Holgura'!$B$6:$B$11,$A29,'Holgura'!$E$6:$E$11,"Ambos")+COUNTIFS('Entrega'!$B$6:$B$9,$A29,'Entrega'!$E$6:$E$9,"Diego")+COUNTIFS('Entrega'!$B$6:$B$9,$A29,'Entrega'!$E$6:$E$9,"Ambos")+COUNTIFS('Defensa'!$B$6:$B$10,$A29,'Defensa'!$E$6:$E$10,"Diego")+COUNTIFS('Defensa'!$B$6:$B$10,$A29,'Defensa'!$E$6:$E$10,"Ambos")</f>
+        <f>COUNTIFS('S1'!$B$6:$B$32,$A29,'S1'!$E$6:$E$32,"Diego")+COUNTIFS('S1'!$B$6:$B$32,$A29,'S1'!$E$6:$E$32,"Ambos")+COUNTIFS('S2'!$B$6:$B$23,$A29,'S2'!$E$6:$E$23,"Diego")+COUNTIFS('S2'!$B$6:$B$23,$A29,'S2'!$E$6:$E$23,"Ambos")+COUNTIFS('S3'!$B$6:$B$24,$A29,'S3'!$E$6:$E$24,"Diego")+COUNTIFS('S3'!$B$6:$B$24,$A29,'S3'!$E$6:$E$24,"Ambos")+COUNTIFS('S4'!$B$6:$B$22,$A29,'S4'!$E$6:$E$22,"Diego")+COUNTIFS('S4'!$B$6:$B$22,$A29,'S4'!$E$6:$E$22,"Ambos")+COUNTIFS('S5'!$B$6:$B$20,$A29,'S5'!$E$6:$E$20,"Diego")+COUNTIFS('S5'!$B$6:$B$20,$A29,'S5'!$E$6:$E$20,"Ambos")+COUNTIFS('S6'!$B$6:$B$17,$A29,'S6'!$E$6:$E$17,"Diego")+COUNTIFS('S6'!$B$6:$B$17,$A29,'S6'!$E$6:$E$17,"Ambos")+COUNTIFS('S7'!$B$6:$B$19,$A29,'S7'!$E$6:$E$19,"Diego")+COUNTIFS('S7'!$B$6:$B$19,$A29,'S7'!$E$6:$E$19,"Ambos")+COUNTIFS('S8'!$B$6:$B$23,$A29,'S8'!$E$6:$E$23,"Diego")+COUNTIFS('S8'!$B$6:$B$23,$A29,'S8'!$E$6:$E$23,"Ambos")+COUNTIFS('S9'!$B$6:$B$15,$A29,'S9'!$E$6:$E$15,"Diego")+COUNTIFS('S9'!$B$6:$B$15,$A29,'S9'!$E$6:$E$15,"Ambos")+COUNTIFS('S10'!$B$6:$B$13,$A29,'S10'!$E$6:$E$13,"Diego")+COUNTIFS('S10'!$B$6:$B$13,$A29,'S10'!$E$6:$E$13,"Ambos")+COUNTIFS('Holgura'!$B$6:$B$11,$A29,'Holgura'!$E$6:$E$11,"Diego")+COUNTIFS('Holgura'!$B$6:$B$11,$A29,'Holgura'!$E$6:$E$11,"Ambos")+COUNTIFS('Entrega'!$B$6:$B$9,$A29,'Entrega'!$E$6:$E$9,"Diego")+COUNTIFS('Entrega'!$B$6:$B$9,$A29,'Entrega'!$E$6:$E$9,"Ambos")+COUNTIFS('Defensa'!$B$6:$B$10,$A29,'Defensa'!$E$6:$E$10,"Diego")+COUNTIFS('Defensa'!$B$6:$B$10,$A29,'Defensa'!$E$6:$E$10,"Ambos")</f>
         <v/>
       </c>
     </row>
@@ -9405,19 +9426,19 @@
         <v/>
       </c>
       <c r="D30" s="21">
-        <f>SUMIFS('S1'!$I$6:$I$32,'S1'!$B$6:$B$32,$A30,'S1'!$E$6:$E$32,"Víctor")+SUMIFS('S1'!$I$6:$I$32,'S1'!$B$6:$B$32,$A30,'S1'!$E$6:$E$32,"Ambos")+SUMIFS('S2'!$I$6:$I$23,'S2'!$B$6:$B$23,$A30,'S2'!$E$6:$E$23,"Víctor")+SUMIFS('S2'!$I$6:$I$23,'S2'!$B$6:$B$23,$A30,'S2'!$E$6:$E$23,"Ambos")+SUMIFS('S3'!$I$6:$I$19,'S3'!$B$6:$B$19,$A30,'S3'!$E$6:$E$19,"Víctor")+SUMIFS('S3'!$I$6:$I$19,'S3'!$B$6:$B$19,$A30,'S3'!$E$6:$E$19,"Ambos")+SUMIFS('S4'!$I$6:$I$20,'S4'!$B$6:$B$20,$A30,'S4'!$E$6:$E$20,"Víctor")+SUMIFS('S4'!$I$6:$I$20,'S4'!$B$6:$B$20,$A30,'S4'!$E$6:$E$20,"Ambos")+SUMIFS('S5'!$I$6:$I$20,'S5'!$B$6:$B$20,$A30,'S5'!$E$6:$E$20,"Víctor")+SUMIFS('S5'!$I$6:$I$20,'S5'!$B$6:$B$20,$A30,'S5'!$E$6:$E$20,"Ambos")+SUMIFS('S6'!$I$6:$I$17,'S6'!$B$6:$B$17,$A30,'S6'!$E$6:$E$17,"Víctor")+SUMIFS('S6'!$I$6:$I$17,'S6'!$B$6:$B$17,$A30,'S6'!$E$6:$E$17,"Ambos")+SUMIFS('S7'!$I$6:$I$19,'S7'!$B$6:$B$19,$A30,'S7'!$E$6:$E$19,"Víctor")+SUMIFS('S7'!$I$6:$I$19,'S7'!$B$6:$B$19,$A30,'S7'!$E$6:$E$19,"Ambos")+SUMIFS('S8'!$I$6:$I$23,'S8'!$B$6:$B$23,$A30,'S8'!$E$6:$E$23,"Víctor")+SUMIFS('S8'!$I$6:$I$23,'S8'!$B$6:$B$23,$A30,'S8'!$E$6:$E$23,"Ambos")+SUMIFS('S9'!$I$6:$I$15,'S9'!$B$6:$B$15,$A30,'S9'!$E$6:$E$15,"Víctor")+SUMIFS('S9'!$I$6:$I$15,'S9'!$B$6:$B$15,$A30,'S9'!$E$6:$E$15,"Ambos")+SUMIFS('S10'!$I$6:$I$13,'S10'!$B$6:$B$13,$A30,'S10'!$E$6:$E$13,"Víctor")+SUMIFS('S10'!$I$6:$I$13,'S10'!$B$6:$B$13,$A30,'S10'!$E$6:$E$13,"Ambos")+SUMIFS('Holgura'!$I$6:$I$11,'Holgura'!$B$6:$B$11,$A30,'Holgura'!$E$6:$E$11,"Víctor")+SUMIFS('Holgura'!$I$6:$I$11,'Holgura'!$B$6:$B$11,$A30,'Holgura'!$E$6:$E$11,"Ambos")+SUMIFS('Entrega'!$I$6:$I$9,'Entrega'!$B$6:$B$9,$A30,'Entrega'!$E$6:$E$9,"Víctor")+SUMIFS('Entrega'!$I$6:$I$9,'Entrega'!$B$6:$B$9,$A30,'Entrega'!$E$6:$E$9,"Ambos")+SUMIFS('Defensa'!$I$6:$I$10,'Defensa'!$B$6:$B$10,$A30,'Defensa'!$E$6:$E$10,"Víctor")+SUMIFS('Defensa'!$I$6:$I$10,'Defensa'!$B$6:$B$10,$A30,'Defensa'!$E$6:$E$10,"Ambos")</f>
+        <f>SUMIFS('S1'!$I$6:$I$32,'S1'!$B$6:$B$32,$A30,'S1'!$E$6:$E$32,"Víctor")+SUMIFS('S1'!$I$6:$I$32,'S1'!$B$6:$B$32,$A30,'S1'!$E$6:$E$32,"Ambos")+SUMIFS('S2'!$I$6:$I$23,'S2'!$B$6:$B$23,$A30,'S2'!$E$6:$E$23,"Víctor")+SUMIFS('S2'!$I$6:$I$23,'S2'!$B$6:$B$23,$A30,'S2'!$E$6:$E$23,"Ambos")+SUMIFS('S3'!$I$6:$I$24,'S3'!$B$6:$B$24,$A30,'S3'!$E$6:$E$24,"Víctor")+SUMIFS('S3'!$I$6:$I$24,'S3'!$B$6:$B$24,$A30,'S3'!$E$6:$E$24,"Ambos")+SUMIFS('S4'!$I$6:$I$22,'S4'!$B$6:$B$22,$A30,'S4'!$E$6:$E$22,"Víctor")+SUMIFS('S4'!$I$6:$I$22,'S4'!$B$6:$B$22,$A30,'S4'!$E$6:$E$22,"Ambos")+SUMIFS('S5'!$I$6:$I$20,'S5'!$B$6:$B$20,$A30,'S5'!$E$6:$E$20,"Víctor")+SUMIFS('S5'!$I$6:$I$20,'S5'!$B$6:$B$20,$A30,'S5'!$E$6:$E$20,"Ambos")+SUMIFS('S6'!$I$6:$I$17,'S6'!$B$6:$B$17,$A30,'S6'!$E$6:$E$17,"Víctor")+SUMIFS('S6'!$I$6:$I$17,'S6'!$B$6:$B$17,$A30,'S6'!$E$6:$E$17,"Ambos")+SUMIFS('S7'!$I$6:$I$19,'S7'!$B$6:$B$19,$A30,'S7'!$E$6:$E$19,"Víctor")+SUMIFS('S7'!$I$6:$I$19,'S7'!$B$6:$B$19,$A30,'S7'!$E$6:$E$19,"Ambos")+SUMIFS('S8'!$I$6:$I$23,'S8'!$B$6:$B$23,$A30,'S8'!$E$6:$E$23,"Víctor")+SUMIFS('S8'!$I$6:$I$23,'S8'!$B$6:$B$23,$A30,'S8'!$E$6:$E$23,"Ambos")+SUMIFS('S9'!$I$6:$I$15,'S9'!$B$6:$B$15,$A30,'S9'!$E$6:$E$15,"Víctor")+SUMIFS('S9'!$I$6:$I$15,'S9'!$B$6:$B$15,$A30,'S9'!$E$6:$E$15,"Ambos")+SUMIFS('S10'!$I$6:$I$13,'S10'!$B$6:$B$13,$A30,'S10'!$E$6:$E$13,"Víctor")+SUMIFS('S10'!$I$6:$I$13,'S10'!$B$6:$B$13,$A30,'S10'!$E$6:$E$13,"Ambos")+SUMIFS('Holgura'!$I$6:$I$11,'Holgura'!$B$6:$B$11,$A30,'Holgura'!$E$6:$E$11,"Víctor")+SUMIFS('Holgura'!$I$6:$I$11,'Holgura'!$B$6:$B$11,$A30,'Holgura'!$E$6:$E$11,"Ambos")+SUMIFS('Entrega'!$I$6:$I$9,'Entrega'!$B$6:$B$9,$A30,'Entrega'!$E$6:$E$9,"Víctor")+SUMIFS('Entrega'!$I$6:$I$9,'Entrega'!$B$6:$B$9,$A30,'Entrega'!$E$6:$E$9,"Ambos")+SUMIFS('Defensa'!$I$6:$I$10,'Defensa'!$B$6:$B$10,$A30,'Defensa'!$E$6:$E$10,"Víctor")+SUMIFS('Defensa'!$I$6:$I$10,'Defensa'!$B$6:$B$10,$A30,'Defensa'!$E$6:$E$10,"Ambos")</f>
         <v/>
       </c>
       <c r="E30" s="21">
-        <f>SUMIFS('S1'!$I$6:$I$32,'S1'!$B$6:$B$32,$A30,'S1'!$E$6:$E$32,"Diego")+SUMIFS('S1'!$I$6:$I$32,'S1'!$B$6:$B$32,$A30,'S1'!$E$6:$E$32,"Ambos")+SUMIFS('S2'!$I$6:$I$23,'S2'!$B$6:$B$23,$A30,'S2'!$E$6:$E$23,"Diego")+SUMIFS('S2'!$I$6:$I$23,'S2'!$B$6:$B$23,$A30,'S2'!$E$6:$E$23,"Ambos")+SUMIFS('S3'!$I$6:$I$19,'S3'!$B$6:$B$19,$A30,'S3'!$E$6:$E$19,"Diego")+SUMIFS('S3'!$I$6:$I$19,'S3'!$B$6:$B$19,$A30,'S3'!$E$6:$E$19,"Ambos")+SUMIFS('S4'!$I$6:$I$20,'S4'!$B$6:$B$20,$A30,'S4'!$E$6:$E$20,"Diego")+SUMIFS('S4'!$I$6:$I$20,'S4'!$B$6:$B$20,$A30,'S4'!$E$6:$E$20,"Ambos")+SUMIFS('S5'!$I$6:$I$20,'S5'!$B$6:$B$20,$A30,'S5'!$E$6:$E$20,"Diego")+SUMIFS('S5'!$I$6:$I$20,'S5'!$B$6:$B$20,$A30,'S5'!$E$6:$E$20,"Ambos")+SUMIFS('S6'!$I$6:$I$17,'S6'!$B$6:$B$17,$A30,'S6'!$E$6:$E$17,"Diego")+SUMIFS('S6'!$I$6:$I$17,'S6'!$B$6:$B$17,$A30,'S6'!$E$6:$E$17,"Ambos")+SUMIFS('S7'!$I$6:$I$19,'S7'!$B$6:$B$19,$A30,'S7'!$E$6:$E$19,"Diego")+SUMIFS('S7'!$I$6:$I$19,'S7'!$B$6:$B$19,$A30,'S7'!$E$6:$E$19,"Ambos")+SUMIFS('S8'!$I$6:$I$23,'S8'!$B$6:$B$23,$A30,'S8'!$E$6:$E$23,"Diego")+SUMIFS('S8'!$I$6:$I$23,'S8'!$B$6:$B$23,$A30,'S8'!$E$6:$E$23,"Ambos")+SUMIFS('S9'!$I$6:$I$15,'S9'!$B$6:$B$15,$A30,'S9'!$E$6:$E$15,"Diego")+SUMIFS('S9'!$I$6:$I$15,'S9'!$B$6:$B$15,$A30,'S9'!$E$6:$E$15,"Ambos")+SUMIFS('S10'!$I$6:$I$13,'S10'!$B$6:$B$13,$A30,'S10'!$E$6:$E$13,"Diego")+SUMIFS('S10'!$I$6:$I$13,'S10'!$B$6:$B$13,$A30,'S10'!$E$6:$E$13,"Ambos")+SUMIFS('Holgura'!$I$6:$I$11,'Holgura'!$B$6:$B$11,$A30,'Holgura'!$E$6:$E$11,"Diego")+SUMIFS('Holgura'!$I$6:$I$11,'Holgura'!$B$6:$B$11,$A30,'Holgura'!$E$6:$E$11,"Ambos")+SUMIFS('Entrega'!$I$6:$I$9,'Entrega'!$B$6:$B$9,$A30,'Entrega'!$E$6:$E$9,"Diego")+SUMIFS('Entrega'!$I$6:$I$9,'Entrega'!$B$6:$B$9,$A30,'Entrega'!$E$6:$E$9,"Ambos")+SUMIFS('Defensa'!$I$6:$I$10,'Defensa'!$B$6:$B$10,$A30,'Defensa'!$E$6:$E$10,"Diego")+SUMIFS('Defensa'!$I$6:$I$10,'Defensa'!$B$6:$B$10,$A30,'Defensa'!$E$6:$E$10,"Ambos")</f>
+        <f>SUMIFS('S1'!$I$6:$I$32,'S1'!$B$6:$B$32,$A30,'S1'!$E$6:$E$32,"Diego")+SUMIFS('S1'!$I$6:$I$32,'S1'!$B$6:$B$32,$A30,'S1'!$E$6:$E$32,"Ambos")+SUMIFS('S2'!$I$6:$I$23,'S2'!$B$6:$B$23,$A30,'S2'!$E$6:$E$23,"Diego")+SUMIFS('S2'!$I$6:$I$23,'S2'!$B$6:$B$23,$A30,'S2'!$E$6:$E$23,"Ambos")+SUMIFS('S3'!$I$6:$I$24,'S3'!$B$6:$B$24,$A30,'S3'!$E$6:$E$24,"Diego")+SUMIFS('S3'!$I$6:$I$24,'S3'!$B$6:$B$24,$A30,'S3'!$E$6:$E$24,"Ambos")+SUMIFS('S4'!$I$6:$I$22,'S4'!$B$6:$B$22,$A30,'S4'!$E$6:$E$22,"Diego")+SUMIFS('S4'!$I$6:$I$22,'S4'!$B$6:$B$22,$A30,'S4'!$E$6:$E$22,"Ambos")+SUMIFS('S5'!$I$6:$I$20,'S5'!$B$6:$B$20,$A30,'S5'!$E$6:$E$20,"Diego")+SUMIFS('S5'!$I$6:$I$20,'S5'!$B$6:$B$20,$A30,'S5'!$E$6:$E$20,"Ambos")+SUMIFS('S6'!$I$6:$I$17,'S6'!$B$6:$B$17,$A30,'S6'!$E$6:$E$17,"Diego")+SUMIFS('S6'!$I$6:$I$17,'S6'!$B$6:$B$17,$A30,'S6'!$E$6:$E$17,"Ambos")+SUMIFS('S7'!$I$6:$I$19,'S7'!$B$6:$B$19,$A30,'S7'!$E$6:$E$19,"Diego")+SUMIFS('S7'!$I$6:$I$19,'S7'!$B$6:$B$19,$A30,'S7'!$E$6:$E$19,"Ambos")+SUMIFS('S8'!$I$6:$I$23,'S8'!$B$6:$B$23,$A30,'S8'!$E$6:$E$23,"Diego")+SUMIFS('S8'!$I$6:$I$23,'S8'!$B$6:$B$23,$A30,'S8'!$E$6:$E$23,"Ambos")+SUMIFS('S9'!$I$6:$I$15,'S9'!$B$6:$B$15,$A30,'S9'!$E$6:$E$15,"Diego")+SUMIFS('S9'!$I$6:$I$15,'S9'!$B$6:$B$15,$A30,'S9'!$E$6:$E$15,"Ambos")+SUMIFS('S10'!$I$6:$I$13,'S10'!$B$6:$B$13,$A30,'S10'!$E$6:$E$13,"Diego")+SUMIFS('S10'!$I$6:$I$13,'S10'!$B$6:$B$13,$A30,'S10'!$E$6:$E$13,"Ambos")+SUMIFS('Holgura'!$I$6:$I$11,'Holgura'!$B$6:$B$11,$A30,'Holgura'!$E$6:$E$11,"Diego")+SUMIFS('Holgura'!$I$6:$I$11,'Holgura'!$B$6:$B$11,$A30,'Holgura'!$E$6:$E$11,"Ambos")+SUMIFS('Entrega'!$I$6:$I$9,'Entrega'!$B$6:$B$9,$A30,'Entrega'!$E$6:$E$9,"Diego")+SUMIFS('Entrega'!$I$6:$I$9,'Entrega'!$B$6:$B$9,$A30,'Entrega'!$E$6:$E$9,"Ambos")+SUMIFS('Defensa'!$I$6:$I$10,'Defensa'!$B$6:$B$10,$A30,'Defensa'!$E$6:$E$10,"Diego")+SUMIFS('Defensa'!$I$6:$I$10,'Defensa'!$B$6:$B$10,$A30,'Defensa'!$E$6:$E$10,"Ambos")</f>
         <v/>
       </c>
       <c r="F30" s="21">
-        <f>COUNTIFS('S1'!$B$6:$B$32,$A30,'S1'!$E$6:$E$32,"Víctor")+COUNTIFS('S1'!$B$6:$B$32,$A30,'S1'!$E$6:$E$32,"Ambos")+COUNTIFS('S2'!$B$6:$B$23,$A30,'S2'!$E$6:$E$23,"Víctor")+COUNTIFS('S2'!$B$6:$B$23,$A30,'S2'!$E$6:$E$23,"Ambos")+COUNTIFS('S3'!$B$6:$B$19,$A30,'S3'!$E$6:$E$19,"Víctor")+COUNTIFS('S3'!$B$6:$B$19,$A30,'S3'!$E$6:$E$19,"Ambos")+COUNTIFS('S4'!$B$6:$B$20,$A30,'S4'!$E$6:$E$20,"Víctor")+COUNTIFS('S4'!$B$6:$B$20,$A30,'S4'!$E$6:$E$20,"Ambos")+COUNTIFS('S5'!$B$6:$B$20,$A30,'S5'!$E$6:$E$20,"Víctor")+COUNTIFS('S5'!$B$6:$B$20,$A30,'S5'!$E$6:$E$20,"Ambos")+COUNTIFS('S6'!$B$6:$B$17,$A30,'S6'!$E$6:$E$17,"Víctor")+COUNTIFS('S6'!$B$6:$B$17,$A30,'S6'!$E$6:$E$17,"Ambos")+COUNTIFS('S7'!$B$6:$B$19,$A30,'S7'!$E$6:$E$19,"Víctor")+COUNTIFS('S7'!$B$6:$B$19,$A30,'S7'!$E$6:$E$19,"Ambos")+COUNTIFS('S8'!$B$6:$B$23,$A30,'S8'!$E$6:$E$23,"Víctor")+COUNTIFS('S8'!$B$6:$B$23,$A30,'S8'!$E$6:$E$23,"Ambos")+COUNTIFS('S9'!$B$6:$B$15,$A30,'S9'!$E$6:$E$15,"Víctor")+COUNTIFS('S9'!$B$6:$B$15,$A30,'S9'!$E$6:$E$15,"Ambos")+COUNTIFS('S10'!$B$6:$B$13,$A30,'S10'!$E$6:$E$13,"Víctor")+COUNTIFS('S10'!$B$6:$B$13,$A30,'S10'!$E$6:$E$13,"Ambos")+COUNTIFS('Holgura'!$B$6:$B$11,$A30,'Holgura'!$E$6:$E$11,"Víctor")+COUNTIFS('Holgura'!$B$6:$B$11,$A30,'Holgura'!$E$6:$E$11,"Ambos")+COUNTIFS('Entrega'!$B$6:$B$9,$A30,'Entrega'!$E$6:$E$9,"Víctor")+COUNTIFS('Entrega'!$B$6:$B$9,$A30,'Entrega'!$E$6:$E$9,"Ambos")+COUNTIFS('Defensa'!$B$6:$B$10,$A30,'Defensa'!$E$6:$E$10,"Víctor")+COUNTIFS('Defensa'!$B$6:$B$10,$A30,'Defensa'!$E$6:$E$10,"Ambos")</f>
+        <f>COUNTIFS('S1'!$B$6:$B$32,$A30,'S1'!$E$6:$E$32,"Víctor")+COUNTIFS('S1'!$B$6:$B$32,$A30,'S1'!$E$6:$E$32,"Ambos")+COUNTIFS('S2'!$B$6:$B$23,$A30,'S2'!$E$6:$E$23,"Víctor")+COUNTIFS('S2'!$B$6:$B$23,$A30,'S2'!$E$6:$E$23,"Ambos")+COUNTIFS('S3'!$B$6:$B$24,$A30,'S3'!$E$6:$E$24,"Víctor")+COUNTIFS('S3'!$B$6:$B$24,$A30,'S3'!$E$6:$E$24,"Ambos")+COUNTIFS('S4'!$B$6:$B$22,$A30,'S4'!$E$6:$E$22,"Víctor")+COUNTIFS('S4'!$B$6:$B$22,$A30,'S4'!$E$6:$E$22,"Ambos")+COUNTIFS('S5'!$B$6:$B$20,$A30,'S5'!$E$6:$E$20,"Víctor")+COUNTIFS('S5'!$B$6:$B$20,$A30,'S5'!$E$6:$E$20,"Ambos")+COUNTIFS('S6'!$B$6:$B$17,$A30,'S6'!$E$6:$E$17,"Víctor")+COUNTIFS('S6'!$B$6:$B$17,$A30,'S6'!$E$6:$E$17,"Ambos")+COUNTIFS('S7'!$B$6:$B$19,$A30,'S7'!$E$6:$E$19,"Víctor")+COUNTIFS('S7'!$B$6:$B$19,$A30,'S7'!$E$6:$E$19,"Ambos")+COUNTIFS('S8'!$B$6:$B$23,$A30,'S8'!$E$6:$E$23,"Víctor")+COUNTIFS('S8'!$B$6:$B$23,$A30,'S8'!$E$6:$E$23,"Ambos")+COUNTIFS('S9'!$B$6:$B$15,$A30,'S9'!$E$6:$E$15,"Víctor")+COUNTIFS('S9'!$B$6:$B$15,$A30,'S9'!$E$6:$E$15,"Ambos")+COUNTIFS('S10'!$B$6:$B$13,$A30,'S10'!$E$6:$E$13,"Víctor")+COUNTIFS('S10'!$B$6:$B$13,$A30,'S10'!$E$6:$E$13,"Ambos")+COUNTIFS('Holgura'!$B$6:$B$11,$A30,'Holgura'!$E$6:$E$11,"Víctor")+COUNTIFS('Holgura'!$B$6:$B$11,$A30,'Holgura'!$E$6:$E$11,"Ambos")+COUNTIFS('Entrega'!$B$6:$B$9,$A30,'Entrega'!$E$6:$E$9,"Víctor")+COUNTIFS('Entrega'!$B$6:$B$9,$A30,'Entrega'!$E$6:$E$9,"Ambos")+COUNTIFS('Defensa'!$B$6:$B$10,$A30,'Defensa'!$E$6:$E$10,"Víctor")+COUNTIFS('Defensa'!$B$6:$B$10,$A30,'Defensa'!$E$6:$E$10,"Ambos")</f>
         <v/>
       </c>
       <c r="G30" s="21">
-        <f>COUNTIFS('S1'!$B$6:$B$32,$A30,'S1'!$E$6:$E$32,"Diego")+COUNTIFS('S1'!$B$6:$B$32,$A30,'S1'!$E$6:$E$32,"Ambos")+COUNTIFS('S2'!$B$6:$B$23,$A30,'S2'!$E$6:$E$23,"Diego")+COUNTIFS('S2'!$B$6:$B$23,$A30,'S2'!$E$6:$E$23,"Ambos")+COUNTIFS('S3'!$B$6:$B$19,$A30,'S3'!$E$6:$E$19,"Diego")+COUNTIFS('S3'!$B$6:$B$19,$A30,'S3'!$E$6:$E$19,"Ambos")+COUNTIFS('S4'!$B$6:$B$20,$A30,'S4'!$E$6:$E$20,"Diego")+COUNTIFS('S4'!$B$6:$B$20,$A30,'S4'!$E$6:$E$20,"Ambos")+COUNTIFS('S5'!$B$6:$B$20,$A30,'S5'!$E$6:$E$20,"Diego")+COUNTIFS('S5'!$B$6:$B$20,$A30,'S5'!$E$6:$E$20,"Ambos")+COUNTIFS('S6'!$B$6:$B$17,$A30,'S6'!$E$6:$E$17,"Diego")+COUNTIFS('S6'!$B$6:$B$17,$A30,'S6'!$E$6:$E$17,"Ambos")+COUNTIFS('S7'!$B$6:$B$19,$A30,'S7'!$E$6:$E$19,"Diego")+COUNTIFS('S7'!$B$6:$B$19,$A30,'S7'!$E$6:$E$19,"Ambos")+COUNTIFS('S8'!$B$6:$B$23,$A30,'S8'!$E$6:$E$23,"Diego")+COUNTIFS('S8'!$B$6:$B$23,$A30,'S8'!$E$6:$E$23,"Ambos")+COUNTIFS('S9'!$B$6:$B$15,$A30,'S9'!$E$6:$E$15,"Diego")+COUNTIFS('S9'!$B$6:$B$15,$A30,'S9'!$E$6:$E$15,"Ambos")+COUNTIFS('S10'!$B$6:$B$13,$A30,'S10'!$E$6:$E$13,"Diego")+COUNTIFS('S10'!$B$6:$B$13,$A30,'S10'!$E$6:$E$13,"Ambos")+COUNTIFS('Holgura'!$B$6:$B$11,$A30,'Holgura'!$E$6:$E$11,"Diego")+COUNTIFS('Holgura'!$B$6:$B$11,$A30,'Holgura'!$E$6:$E$11,"Ambos")+COUNTIFS('Entrega'!$B$6:$B$9,$A30,'Entrega'!$E$6:$E$9,"Diego")+COUNTIFS('Entrega'!$B$6:$B$9,$A30,'Entrega'!$E$6:$E$9,"Ambos")+COUNTIFS('Defensa'!$B$6:$B$10,$A30,'Defensa'!$E$6:$E$10,"Diego")+COUNTIFS('Defensa'!$B$6:$B$10,$A30,'Defensa'!$E$6:$E$10,"Ambos")</f>
+        <f>COUNTIFS('S1'!$B$6:$B$32,$A30,'S1'!$E$6:$E$32,"Diego")+COUNTIFS('S1'!$B$6:$B$32,$A30,'S1'!$E$6:$E$32,"Ambos")+COUNTIFS('S2'!$B$6:$B$23,$A30,'S2'!$E$6:$E$23,"Diego")+COUNTIFS('S2'!$B$6:$B$23,$A30,'S2'!$E$6:$E$23,"Ambos")+COUNTIFS('S3'!$B$6:$B$24,$A30,'S3'!$E$6:$E$24,"Diego")+COUNTIFS('S3'!$B$6:$B$24,$A30,'S3'!$E$6:$E$24,"Ambos")+COUNTIFS('S4'!$B$6:$B$22,$A30,'S4'!$E$6:$E$22,"Diego")+COUNTIFS('S4'!$B$6:$B$22,$A30,'S4'!$E$6:$E$22,"Ambos")+COUNTIFS('S5'!$B$6:$B$20,$A30,'S5'!$E$6:$E$20,"Diego")+COUNTIFS('S5'!$B$6:$B$20,$A30,'S5'!$E$6:$E$20,"Ambos")+COUNTIFS('S6'!$B$6:$B$17,$A30,'S6'!$E$6:$E$17,"Diego")+COUNTIFS('S6'!$B$6:$B$17,$A30,'S6'!$E$6:$E$17,"Ambos")+COUNTIFS('S7'!$B$6:$B$19,$A30,'S7'!$E$6:$E$19,"Diego")+COUNTIFS('S7'!$B$6:$B$19,$A30,'S7'!$E$6:$E$19,"Ambos")+COUNTIFS('S8'!$B$6:$B$23,$A30,'S8'!$E$6:$E$23,"Diego")+COUNTIFS('S8'!$B$6:$B$23,$A30,'S8'!$E$6:$E$23,"Ambos")+COUNTIFS('S9'!$B$6:$B$15,$A30,'S9'!$E$6:$E$15,"Diego")+COUNTIFS('S9'!$B$6:$B$15,$A30,'S9'!$E$6:$E$15,"Ambos")+COUNTIFS('S10'!$B$6:$B$13,$A30,'S10'!$E$6:$E$13,"Diego")+COUNTIFS('S10'!$B$6:$B$13,$A30,'S10'!$E$6:$E$13,"Ambos")+COUNTIFS('Holgura'!$B$6:$B$11,$A30,'Holgura'!$E$6:$E$11,"Diego")+COUNTIFS('Holgura'!$B$6:$B$11,$A30,'Holgura'!$E$6:$E$11,"Ambos")+COUNTIFS('Entrega'!$B$6:$B$9,$A30,'Entrega'!$E$6:$E$9,"Diego")+COUNTIFS('Entrega'!$B$6:$B$9,$A30,'Entrega'!$E$6:$E$9,"Ambos")+COUNTIFS('Defensa'!$B$6:$B$10,$A30,'Defensa'!$E$6:$E$10,"Diego")+COUNTIFS('Defensa'!$B$6:$B$10,$A30,'Defensa'!$E$6:$E$10,"Ambos")</f>
         <v/>
       </c>
     </row>
@@ -9434,19 +9455,19 @@
         <v/>
       </c>
       <c r="D31" s="21">
-        <f>SUMIFS('S1'!$I$6:$I$32,'S1'!$B$6:$B$32,$A31,'S1'!$E$6:$E$32,"Víctor")+SUMIFS('S1'!$I$6:$I$32,'S1'!$B$6:$B$32,$A31,'S1'!$E$6:$E$32,"Ambos")+SUMIFS('S2'!$I$6:$I$23,'S2'!$B$6:$B$23,$A31,'S2'!$E$6:$E$23,"Víctor")+SUMIFS('S2'!$I$6:$I$23,'S2'!$B$6:$B$23,$A31,'S2'!$E$6:$E$23,"Ambos")+SUMIFS('S3'!$I$6:$I$19,'S3'!$B$6:$B$19,$A31,'S3'!$E$6:$E$19,"Víctor")+SUMIFS('S3'!$I$6:$I$19,'S3'!$B$6:$B$19,$A31,'S3'!$E$6:$E$19,"Ambos")+SUMIFS('S4'!$I$6:$I$20,'S4'!$B$6:$B$20,$A31,'S4'!$E$6:$E$20,"Víctor")+SUMIFS('S4'!$I$6:$I$20,'S4'!$B$6:$B$20,$A31,'S4'!$E$6:$E$20,"Ambos")+SUMIFS('S5'!$I$6:$I$20,'S5'!$B$6:$B$20,$A31,'S5'!$E$6:$E$20,"Víctor")+SUMIFS('S5'!$I$6:$I$20,'S5'!$B$6:$B$20,$A31,'S5'!$E$6:$E$20,"Ambos")+SUMIFS('S6'!$I$6:$I$17,'S6'!$B$6:$B$17,$A31,'S6'!$E$6:$E$17,"Víctor")+SUMIFS('S6'!$I$6:$I$17,'S6'!$B$6:$B$17,$A31,'S6'!$E$6:$E$17,"Ambos")+SUMIFS('S7'!$I$6:$I$19,'S7'!$B$6:$B$19,$A31,'S7'!$E$6:$E$19,"Víctor")+SUMIFS('S7'!$I$6:$I$19,'S7'!$B$6:$B$19,$A31,'S7'!$E$6:$E$19,"Ambos")+SUMIFS('S8'!$I$6:$I$23,'S8'!$B$6:$B$23,$A31,'S8'!$E$6:$E$23,"Víctor")+SUMIFS('S8'!$I$6:$I$23,'S8'!$B$6:$B$23,$A31,'S8'!$E$6:$E$23,"Ambos")+SUMIFS('S9'!$I$6:$I$15,'S9'!$B$6:$B$15,$A31,'S9'!$E$6:$E$15,"Víctor")+SUMIFS('S9'!$I$6:$I$15,'S9'!$B$6:$B$15,$A31,'S9'!$E$6:$E$15,"Ambos")+SUMIFS('S10'!$I$6:$I$13,'S10'!$B$6:$B$13,$A31,'S10'!$E$6:$E$13,"Víctor")+SUMIFS('S10'!$I$6:$I$13,'S10'!$B$6:$B$13,$A31,'S10'!$E$6:$E$13,"Ambos")+SUMIFS('Holgura'!$I$6:$I$11,'Holgura'!$B$6:$B$11,$A31,'Holgura'!$E$6:$E$11,"Víctor")+SUMIFS('Holgura'!$I$6:$I$11,'Holgura'!$B$6:$B$11,$A31,'Holgura'!$E$6:$E$11,"Ambos")+SUMIFS('Entrega'!$I$6:$I$9,'Entrega'!$B$6:$B$9,$A31,'Entrega'!$E$6:$E$9,"Víctor")+SUMIFS('Entrega'!$I$6:$I$9,'Entrega'!$B$6:$B$9,$A31,'Entrega'!$E$6:$E$9,"Ambos")+SUMIFS('Defensa'!$I$6:$I$10,'Defensa'!$B$6:$B$10,$A31,'Defensa'!$E$6:$E$10,"Víctor")+SUMIFS('Defensa'!$I$6:$I$10,'Defensa'!$B$6:$B$10,$A31,'Defensa'!$E$6:$E$10,"Ambos")</f>
+        <f>SUMIFS('S1'!$I$6:$I$32,'S1'!$B$6:$B$32,$A31,'S1'!$E$6:$E$32,"Víctor")+SUMIFS('S1'!$I$6:$I$32,'S1'!$B$6:$B$32,$A31,'S1'!$E$6:$E$32,"Ambos")+SUMIFS('S2'!$I$6:$I$23,'S2'!$B$6:$B$23,$A31,'S2'!$E$6:$E$23,"Víctor")+SUMIFS('S2'!$I$6:$I$23,'S2'!$B$6:$B$23,$A31,'S2'!$E$6:$E$23,"Ambos")+SUMIFS('S3'!$I$6:$I$24,'S3'!$B$6:$B$24,$A31,'S3'!$E$6:$E$24,"Víctor")+SUMIFS('S3'!$I$6:$I$24,'S3'!$B$6:$B$24,$A31,'S3'!$E$6:$E$24,"Ambos")+SUMIFS('S4'!$I$6:$I$22,'S4'!$B$6:$B$22,$A31,'S4'!$E$6:$E$22,"Víctor")+SUMIFS('S4'!$I$6:$I$22,'S4'!$B$6:$B$22,$A31,'S4'!$E$6:$E$22,"Ambos")+SUMIFS('S5'!$I$6:$I$20,'S5'!$B$6:$B$20,$A31,'S5'!$E$6:$E$20,"Víctor")+SUMIFS('S5'!$I$6:$I$20,'S5'!$B$6:$B$20,$A31,'S5'!$E$6:$E$20,"Ambos")+SUMIFS('S6'!$I$6:$I$17,'S6'!$B$6:$B$17,$A31,'S6'!$E$6:$E$17,"Víctor")+SUMIFS('S6'!$I$6:$I$17,'S6'!$B$6:$B$17,$A31,'S6'!$E$6:$E$17,"Ambos")+SUMIFS('S7'!$I$6:$I$19,'S7'!$B$6:$B$19,$A31,'S7'!$E$6:$E$19,"Víctor")+SUMIFS('S7'!$I$6:$I$19,'S7'!$B$6:$B$19,$A31,'S7'!$E$6:$E$19,"Ambos")+SUMIFS('S8'!$I$6:$I$23,'S8'!$B$6:$B$23,$A31,'S8'!$E$6:$E$23,"Víctor")+SUMIFS('S8'!$I$6:$I$23,'S8'!$B$6:$B$23,$A31,'S8'!$E$6:$E$23,"Ambos")+SUMIFS('S9'!$I$6:$I$15,'S9'!$B$6:$B$15,$A31,'S9'!$E$6:$E$15,"Víctor")+SUMIFS('S9'!$I$6:$I$15,'S9'!$B$6:$B$15,$A31,'S9'!$E$6:$E$15,"Ambos")+SUMIFS('S10'!$I$6:$I$13,'S10'!$B$6:$B$13,$A31,'S10'!$E$6:$E$13,"Víctor")+SUMIFS('S10'!$I$6:$I$13,'S10'!$B$6:$B$13,$A31,'S10'!$E$6:$E$13,"Ambos")+SUMIFS('Holgura'!$I$6:$I$11,'Holgura'!$B$6:$B$11,$A31,'Holgura'!$E$6:$E$11,"Víctor")+SUMIFS('Holgura'!$I$6:$I$11,'Holgura'!$B$6:$B$11,$A31,'Holgura'!$E$6:$E$11,"Ambos")+SUMIFS('Entrega'!$I$6:$I$9,'Entrega'!$B$6:$B$9,$A31,'Entrega'!$E$6:$E$9,"Víctor")+SUMIFS('Entrega'!$I$6:$I$9,'Entrega'!$B$6:$B$9,$A31,'Entrega'!$E$6:$E$9,"Ambos")+SUMIFS('Defensa'!$I$6:$I$10,'Defensa'!$B$6:$B$10,$A31,'Defensa'!$E$6:$E$10,"Víctor")+SUMIFS('Defensa'!$I$6:$I$10,'Defensa'!$B$6:$B$10,$A31,'Defensa'!$E$6:$E$10,"Ambos")</f>
         <v/>
       </c>
       <c r="E31" s="21">
-        <f>SUMIFS('S1'!$I$6:$I$32,'S1'!$B$6:$B$32,$A31,'S1'!$E$6:$E$32,"Diego")+SUMIFS('S1'!$I$6:$I$32,'S1'!$B$6:$B$32,$A31,'S1'!$E$6:$E$32,"Ambos")+SUMIFS('S2'!$I$6:$I$23,'S2'!$B$6:$B$23,$A31,'S2'!$E$6:$E$23,"Diego")+SUMIFS('S2'!$I$6:$I$23,'S2'!$B$6:$B$23,$A31,'S2'!$E$6:$E$23,"Ambos")+SUMIFS('S3'!$I$6:$I$19,'S3'!$B$6:$B$19,$A31,'S3'!$E$6:$E$19,"Diego")+SUMIFS('S3'!$I$6:$I$19,'S3'!$B$6:$B$19,$A31,'S3'!$E$6:$E$19,"Ambos")+SUMIFS('S4'!$I$6:$I$20,'S4'!$B$6:$B$20,$A31,'S4'!$E$6:$E$20,"Diego")+SUMIFS('S4'!$I$6:$I$20,'S4'!$B$6:$B$20,$A31,'S4'!$E$6:$E$20,"Ambos")+SUMIFS('S5'!$I$6:$I$20,'S5'!$B$6:$B$20,$A31,'S5'!$E$6:$E$20,"Diego")+SUMIFS('S5'!$I$6:$I$20,'S5'!$B$6:$B$20,$A31,'S5'!$E$6:$E$20,"Ambos")+SUMIFS('S6'!$I$6:$I$17,'S6'!$B$6:$B$17,$A31,'S6'!$E$6:$E$17,"Diego")+SUMIFS('S6'!$I$6:$I$17,'S6'!$B$6:$B$17,$A31,'S6'!$E$6:$E$17,"Ambos")+SUMIFS('S7'!$I$6:$I$19,'S7'!$B$6:$B$19,$A31,'S7'!$E$6:$E$19,"Diego")+SUMIFS('S7'!$I$6:$I$19,'S7'!$B$6:$B$19,$A31,'S7'!$E$6:$E$19,"Ambos")+SUMIFS('S8'!$I$6:$I$23,'S8'!$B$6:$B$23,$A31,'S8'!$E$6:$E$23,"Diego")+SUMIFS('S8'!$I$6:$I$23,'S8'!$B$6:$B$23,$A31,'S8'!$E$6:$E$23,"Ambos")+SUMIFS('S9'!$I$6:$I$15,'S9'!$B$6:$B$15,$A31,'S9'!$E$6:$E$15,"Diego")+SUMIFS('S9'!$I$6:$I$15,'S9'!$B$6:$B$15,$A31,'S9'!$E$6:$E$15,"Ambos")+SUMIFS('S10'!$I$6:$I$13,'S10'!$B$6:$B$13,$A31,'S10'!$E$6:$E$13,"Diego")+SUMIFS('S10'!$I$6:$I$13,'S10'!$B$6:$B$13,$A31,'S10'!$E$6:$E$13,"Ambos")+SUMIFS('Holgura'!$I$6:$I$11,'Holgura'!$B$6:$B$11,$A31,'Holgura'!$E$6:$E$11,"Diego")+SUMIFS('Holgura'!$I$6:$I$11,'Holgura'!$B$6:$B$11,$A31,'Holgura'!$E$6:$E$11,"Ambos")+SUMIFS('Entrega'!$I$6:$I$9,'Entrega'!$B$6:$B$9,$A31,'Entrega'!$E$6:$E$9,"Diego")+SUMIFS('Entrega'!$I$6:$I$9,'Entrega'!$B$6:$B$9,$A31,'Entrega'!$E$6:$E$9,"Ambos")+SUMIFS('Defensa'!$I$6:$I$10,'Defensa'!$B$6:$B$10,$A31,'Defensa'!$E$6:$E$10,"Diego")+SUMIFS('Defensa'!$I$6:$I$10,'Defensa'!$B$6:$B$10,$A31,'Defensa'!$E$6:$E$10,"Ambos")</f>
+        <f>SUMIFS('S1'!$I$6:$I$32,'S1'!$B$6:$B$32,$A31,'S1'!$E$6:$E$32,"Diego")+SUMIFS('S1'!$I$6:$I$32,'S1'!$B$6:$B$32,$A31,'S1'!$E$6:$E$32,"Ambos")+SUMIFS('S2'!$I$6:$I$23,'S2'!$B$6:$B$23,$A31,'S2'!$E$6:$E$23,"Diego")+SUMIFS('S2'!$I$6:$I$23,'S2'!$B$6:$B$23,$A31,'S2'!$E$6:$E$23,"Ambos")+SUMIFS('S3'!$I$6:$I$24,'S3'!$B$6:$B$24,$A31,'S3'!$E$6:$E$24,"Diego")+SUMIFS('S3'!$I$6:$I$24,'S3'!$B$6:$B$24,$A31,'S3'!$E$6:$E$24,"Ambos")+SUMIFS('S4'!$I$6:$I$22,'S4'!$B$6:$B$22,$A31,'S4'!$E$6:$E$22,"Diego")+SUMIFS('S4'!$I$6:$I$22,'S4'!$B$6:$B$22,$A31,'S4'!$E$6:$E$22,"Ambos")+SUMIFS('S5'!$I$6:$I$20,'S5'!$B$6:$B$20,$A31,'S5'!$E$6:$E$20,"Diego")+SUMIFS('S5'!$I$6:$I$20,'S5'!$B$6:$B$20,$A31,'S5'!$E$6:$E$20,"Ambos")+SUMIFS('S6'!$I$6:$I$17,'S6'!$B$6:$B$17,$A31,'S6'!$E$6:$E$17,"Diego")+SUMIFS('S6'!$I$6:$I$17,'S6'!$B$6:$B$17,$A31,'S6'!$E$6:$E$17,"Ambos")+SUMIFS('S7'!$I$6:$I$19,'S7'!$B$6:$B$19,$A31,'S7'!$E$6:$E$19,"Diego")+SUMIFS('S7'!$I$6:$I$19,'S7'!$B$6:$B$19,$A31,'S7'!$E$6:$E$19,"Ambos")+SUMIFS('S8'!$I$6:$I$23,'S8'!$B$6:$B$23,$A31,'S8'!$E$6:$E$23,"Diego")+SUMIFS('S8'!$I$6:$I$23,'S8'!$B$6:$B$23,$A31,'S8'!$E$6:$E$23,"Ambos")+SUMIFS('S9'!$I$6:$I$15,'S9'!$B$6:$B$15,$A31,'S9'!$E$6:$E$15,"Diego")+SUMIFS('S9'!$I$6:$I$15,'S9'!$B$6:$B$15,$A31,'S9'!$E$6:$E$15,"Ambos")+SUMIFS('S10'!$I$6:$I$13,'S10'!$B$6:$B$13,$A31,'S10'!$E$6:$E$13,"Diego")+SUMIFS('S10'!$I$6:$I$13,'S10'!$B$6:$B$13,$A31,'S10'!$E$6:$E$13,"Ambos")+SUMIFS('Holgura'!$I$6:$I$11,'Holgura'!$B$6:$B$11,$A31,'Holgura'!$E$6:$E$11,"Diego")+SUMIFS('Holgura'!$I$6:$I$11,'Holgura'!$B$6:$B$11,$A31,'Holgura'!$E$6:$E$11,"Ambos")+SUMIFS('Entrega'!$I$6:$I$9,'Entrega'!$B$6:$B$9,$A31,'Entrega'!$E$6:$E$9,"Diego")+SUMIFS('Entrega'!$I$6:$I$9,'Entrega'!$B$6:$B$9,$A31,'Entrega'!$E$6:$E$9,"Ambos")+SUMIFS('Defensa'!$I$6:$I$10,'Defensa'!$B$6:$B$10,$A31,'Defensa'!$E$6:$E$10,"Diego")+SUMIFS('Defensa'!$I$6:$I$10,'Defensa'!$B$6:$B$10,$A31,'Defensa'!$E$6:$E$10,"Ambos")</f>
         <v/>
       </c>
       <c r="F31" s="21">
-        <f>COUNTIFS('S1'!$B$6:$B$32,$A31,'S1'!$E$6:$E$32,"Víctor")+COUNTIFS('S1'!$B$6:$B$32,$A31,'S1'!$E$6:$E$32,"Ambos")+COUNTIFS('S2'!$B$6:$B$23,$A31,'S2'!$E$6:$E$23,"Víctor")+COUNTIFS('S2'!$B$6:$B$23,$A31,'S2'!$E$6:$E$23,"Ambos")+COUNTIFS('S3'!$B$6:$B$19,$A31,'S3'!$E$6:$E$19,"Víctor")+COUNTIFS('S3'!$B$6:$B$19,$A31,'S3'!$E$6:$E$19,"Ambos")+COUNTIFS('S4'!$B$6:$B$20,$A31,'S4'!$E$6:$E$20,"Víctor")+COUNTIFS('S4'!$B$6:$B$20,$A31,'S4'!$E$6:$E$20,"Ambos")+COUNTIFS('S5'!$B$6:$B$20,$A31,'S5'!$E$6:$E$20,"Víctor")+COUNTIFS('S5'!$B$6:$B$20,$A31,'S5'!$E$6:$E$20,"Ambos")+COUNTIFS('S6'!$B$6:$B$17,$A31,'S6'!$E$6:$E$17,"Víctor")+COUNTIFS('S6'!$B$6:$B$17,$A31,'S6'!$E$6:$E$17,"Ambos")+COUNTIFS('S7'!$B$6:$B$19,$A31,'S7'!$E$6:$E$19,"Víctor")+COUNTIFS('S7'!$B$6:$B$19,$A31,'S7'!$E$6:$E$19,"Ambos")+COUNTIFS('S8'!$B$6:$B$23,$A31,'S8'!$E$6:$E$23,"Víctor")+COUNTIFS('S8'!$B$6:$B$23,$A31,'S8'!$E$6:$E$23,"Ambos")+COUNTIFS('S9'!$B$6:$B$15,$A31,'S9'!$E$6:$E$15,"Víctor")+COUNTIFS('S9'!$B$6:$B$15,$A31,'S9'!$E$6:$E$15,"Ambos")+COUNTIFS('S10'!$B$6:$B$13,$A31,'S10'!$E$6:$E$13,"Víctor")+COUNTIFS('S10'!$B$6:$B$13,$A31,'S10'!$E$6:$E$13,"Ambos")+COUNTIFS('Holgura'!$B$6:$B$11,$A31,'Holgura'!$E$6:$E$11,"Víctor")+COUNTIFS('Holgura'!$B$6:$B$11,$A31,'Holgura'!$E$6:$E$11,"Ambos")+COUNTIFS('Entrega'!$B$6:$B$9,$A31,'Entrega'!$E$6:$E$9,"Víctor")+COUNTIFS('Entrega'!$B$6:$B$9,$A31,'Entrega'!$E$6:$E$9,"Ambos")+COUNTIFS('Defensa'!$B$6:$B$10,$A31,'Defensa'!$E$6:$E$10,"Víctor")+COUNTIFS('Defensa'!$B$6:$B$10,$A31,'Defensa'!$E$6:$E$10,"Ambos")</f>
+        <f>COUNTIFS('S1'!$B$6:$B$32,$A31,'S1'!$E$6:$E$32,"Víctor")+COUNTIFS('S1'!$B$6:$B$32,$A31,'S1'!$E$6:$E$32,"Ambos")+COUNTIFS('S2'!$B$6:$B$23,$A31,'S2'!$E$6:$E$23,"Víctor")+COUNTIFS('S2'!$B$6:$B$23,$A31,'S2'!$E$6:$E$23,"Ambos")+COUNTIFS('S3'!$B$6:$B$24,$A31,'S3'!$E$6:$E$24,"Víctor")+COUNTIFS('S3'!$B$6:$B$24,$A31,'S3'!$E$6:$E$24,"Ambos")+COUNTIFS('S4'!$B$6:$B$22,$A31,'S4'!$E$6:$E$22,"Víctor")+COUNTIFS('S4'!$B$6:$B$22,$A31,'S4'!$E$6:$E$22,"Ambos")+COUNTIFS('S5'!$B$6:$B$20,$A31,'S5'!$E$6:$E$20,"Víctor")+COUNTIFS('S5'!$B$6:$B$20,$A31,'S5'!$E$6:$E$20,"Ambos")+COUNTIFS('S6'!$B$6:$B$17,$A31,'S6'!$E$6:$E$17,"Víctor")+COUNTIFS('S6'!$B$6:$B$17,$A31,'S6'!$E$6:$E$17,"Ambos")+COUNTIFS('S7'!$B$6:$B$19,$A31,'S7'!$E$6:$E$19,"Víctor")+COUNTIFS('S7'!$B$6:$B$19,$A31,'S7'!$E$6:$E$19,"Ambos")+COUNTIFS('S8'!$B$6:$B$23,$A31,'S8'!$E$6:$E$23,"Víctor")+COUNTIFS('S8'!$B$6:$B$23,$A31,'S8'!$E$6:$E$23,"Ambos")+COUNTIFS('S9'!$B$6:$B$15,$A31,'S9'!$E$6:$E$15,"Víctor")+COUNTIFS('S9'!$B$6:$B$15,$A31,'S9'!$E$6:$E$15,"Ambos")+COUNTIFS('S10'!$B$6:$B$13,$A31,'S10'!$E$6:$E$13,"Víctor")+COUNTIFS('S10'!$B$6:$B$13,$A31,'S10'!$E$6:$E$13,"Ambos")+COUNTIFS('Holgura'!$B$6:$B$11,$A31,'Holgura'!$E$6:$E$11,"Víctor")+COUNTIFS('Holgura'!$B$6:$B$11,$A31,'Holgura'!$E$6:$E$11,"Ambos")+COUNTIFS('Entrega'!$B$6:$B$9,$A31,'Entrega'!$E$6:$E$9,"Víctor")+COUNTIFS('Entrega'!$B$6:$B$9,$A31,'Entrega'!$E$6:$E$9,"Ambos")+COUNTIFS('Defensa'!$B$6:$B$10,$A31,'Defensa'!$E$6:$E$10,"Víctor")+COUNTIFS('Defensa'!$B$6:$B$10,$A31,'Defensa'!$E$6:$E$10,"Ambos")</f>
         <v/>
       </c>
       <c r="G31" s="21">
-        <f>COUNTIFS('S1'!$B$6:$B$32,$A31,'S1'!$E$6:$E$32,"Diego")+COUNTIFS('S1'!$B$6:$B$32,$A31,'S1'!$E$6:$E$32,"Ambos")+COUNTIFS('S2'!$B$6:$B$23,$A31,'S2'!$E$6:$E$23,"Diego")+COUNTIFS('S2'!$B$6:$B$23,$A31,'S2'!$E$6:$E$23,"Ambos")+COUNTIFS('S3'!$B$6:$B$19,$A31,'S3'!$E$6:$E$19,"Diego")+COUNTIFS('S3'!$B$6:$B$19,$A31,'S3'!$E$6:$E$19,"Ambos")+COUNTIFS('S4'!$B$6:$B$20,$A31,'S4'!$E$6:$E$20,"Diego")+COUNTIFS('S4'!$B$6:$B$20,$A31,'S4'!$E$6:$E$20,"Ambos")+COUNTIFS('S5'!$B$6:$B$20,$A31,'S5'!$E$6:$E$20,"Diego")+COUNTIFS('S5'!$B$6:$B$20,$A31,'S5'!$E$6:$E$20,"Ambos")+COUNTIFS('S6'!$B$6:$B$17,$A31,'S6'!$E$6:$E$17,"Diego")+COUNTIFS('S6'!$B$6:$B$17,$A31,'S6'!$E$6:$E$17,"Ambos")+COUNTIFS('S7'!$B$6:$B$19,$A31,'S7'!$E$6:$E$19,"Diego")+COUNTIFS('S7'!$B$6:$B$19,$A31,'S7'!$E$6:$E$19,"Ambos")+COUNTIFS('S8'!$B$6:$B$23,$A31,'S8'!$E$6:$E$23,"Diego")+COUNTIFS('S8'!$B$6:$B$23,$A31,'S8'!$E$6:$E$23,"Ambos")+COUNTIFS('S9'!$B$6:$B$15,$A31,'S9'!$E$6:$E$15,"Diego")+COUNTIFS('S9'!$B$6:$B$15,$A31,'S9'!$E$6:$E$15,"Ambos")+COUNTIFS('S10'!$B$6:$B$13,$A31,'S10'!$E$6:$E$13,"Diego")+COUNTIFS('S10'!$B$6:$B$13,$A31,'S10'!$E$6:$E$13,"Ambos")+COUNTIFS('Holgura'!$B$6:$B$11,$A31,'Holgura'!$E$6:$E$11,"Diego")+COUNTIFS('Holgura'!$B$6:$B$11,$A31,'Holgura'!$E$6:$E$11,"Ambos")+COUNTIFS('Entrega'!$B$6:$B$9,$A31,'Entrega'!$E$6:$E$9,"Diego")+COUNTIFS('Entrega'!$B$6:$B$9,$A31,'Entrega'!$E$6:$E$9,"Ambos")+COUNTIFS('Defensa'!$B$6:$B$10,$A31,'Defensa'!$E$6:$E$10,"Diego")+COUNTIFS('Defensa'!$B$6:$B$10,$A31,'Defensa'!$E$6:$E$10,"Ambos")</f>
+        <f>COUNTIFS('S1'!$B$6:$B$32,$A31,'S1'!$E$6:$E$32,"Diego")+COUNTIFS('S1'!$B$6:$B$32,$A31,'S1'!$E$6:$E$32,"Ambos")+COUNTIFS('S2'!$B$6:$B$23,$A31,'S2'!$E$6:$E$23,"Diego")+COUNTIFS('S2'!$B$6:$B$23,$A31,'S2'!$E$6:$E$23,"Ambos")+COUNTIFS('S3'!$B$6:$B$24,$A31,'S3'!$E$6:$E$24,"Diego")+COUNTIFS('S3'!$B$6:$B$24,$A31,'S3'!$E$6:$E$24,"Ambos")+COUNTIFS('S4'!$B$6:$B$22,$A31,'S4'!$E$6:$E$22,"Diego")+COUNTIFS('S4'!$B$6:$B$22,$A31,'S4'!$E$6:$E$22,"Ambos")+COUNTIFS('S5'!$B$6:$B$20,$A31,'S5'!$E$6:$E$20,"Diego")+COUNTIFS('S5'!$B$6:$B$20,$A31,'S5'!$E$6:$E$20,"Ambos")+COUNTIFS('S6'!$B$6:$B$17,$A31,'S6'!$E$6:$E$17,"Diego")+COUNTIFS('S6'!$B$6:$B$17,$A31,'S6'!$E$6:$E$17,"Ambos")+COUNTIFS('S7'!$B$6:$B$19,$A31,'S7'!$E$6:$E$19,"Diego")+COUNTIFS('S7'!$B$6:$B$19,$A31,'S7'!$E$6:$E$19,"Ambos")+COUNTIFS('S8'!$B$6:$B$23,$A31,'S8'!$E$6:$E$23,"Diego")+COUNTIFS('S8'!$B$6:$B$23,$A31,'S8'!$E$6:$E$23,"Ambos")+COUNTIFS('S9'!$B$6:$B$15,$A31,'S9'!$E$6:$E$15,"Diego")+COUNTIFS('S9'!$B$6:$B$15,$A31,'S9'!$E$6:$E$15,"Ambos")+COUNTIFS('S10'!$B$6:$B$13,$A31,'S10'!$E$6:$E$13,"Diego")+COUNTIFS('S10'!$B$6:$B$13,$A31,'S10'!$E$6:$E$13,"Ambos")+COUNTIFS('Holgura'!$B$6:$B$11,$A31,'Holgura'!$E$6:$E$11,"Diego")+COUNTIFS('Holgura'!$B$6:$B$11,$A31,'Holgura'!$E$6:$E$11,"Ambos")+COUNTIFS('Entrega'!$B$6:$B$9,$A31,'Entrega'!$E$6:$E$9,"Diego")+COUNTIFS('Entrega'!$B$6:$B$9,$A31,'Entrega'!$E$6:$E$9,"Ambos")+COUNTIFS('Defensa'!$B$6:$B$10,$A31,'Defensa'!$E$6:$E$10,"Diego")+COUNTIFS('Defensa'!$B$6:$B$10,$A31,'Defensa'!$E$6:$E$10,"Ambos")</f>
         <v/>
       </c>
     </row>
@@ -9463,19 +9484,19 @@
         <v/>
       </c>
       <c r="D32" s="21">
-        <f>SUMIFS('S1'!$I$6:$I$32,'S1'!$B$6:$B$32,$A32,'S1'!$E$6:$E$32,"Víctor")+SUMIFS('S1'!$I$6:$I$32,'S1'!$B$6:$B$32,$A32,'S1'!$E$6:$E$32,"Ambos")+SUMIFS('S2'!$I$6:$I$23,'S2'!$B$6:$B$23,$A32,'S2'!$E$6:$E$23,"Víctor")+SUMIFS('S2'!$I$6:$I$23,'S2'!$B$6:$B$23,$A32,'S2'!$E$6:$E$23,"Ambos")+SUMIFS('S3'!$I$6:$I$19,'S3'!$B$6:$B$19,$A32,'S3'!$E$6:$E$19,"Víctor")+SUMIFS('S3'!$I$6:$I$19,'S3'!$B$6:$B$19,$A32,'S3'!$E$6:$E$19,"Ambos")+SUMIFS('S4'!$I$6:$I$20,'S4'!$B$6:$B$20,$A32,'S4'!$E$6:$E$20,"Víctor")+SUMIFS('S4'!$I$6:$I$20,'S4'!$B$6:$B$20,$A32,'S4'!$E$6:$E$20,"Ambos")+SUMIFS('S5'!$I$6:$I$20,'S5'!$B$6:$B$20,$A32,'S5'!$E$6:$E$20,"Víctor")+SUMIFS('S5'!$I$6:$I$20,'S5'!$B$6:$B$20,$A32,'S5'!$E$6:$E$20,"Ambos")+SUMIFS('S6'!$I$6:$I$17,'S6'!$B$6:$B$17,$A32,'S6'!$E$6:$E$17,"Víctor")+SUMIFS('S6'!$I$6:$I$17,'S6'!$B$6:$B$17,$A32,'S6'!$E$6:$E$17,"Ambos")+SUMIFS('S7'!$I$6:$I$19,'S7'!$B$6:$B$19,$A32,'S7'!$E$6:$E$19,"Víctor")+SUMIFS('S7'!$I$6:$I$19,'S7'!$B$6:$B$19,$A32,'S7'!$E$6:$E$19,"Ambos")+SUMIFS('S8'!$I$6:$I$23,'S8'!$B$6:$B$23,$A32,'S8'!$E$6:$E$23,"Víctor")+SUMIFS('S8'!$I$6:$I$23,'S8'!$B$6:$B$23,$A32,'S8'!$E$6:$E$23,"Ambos")+SUMIFS('S9'!$I$6:$I$15,'S9'!$B$6:$B$15,$A32,'S9'!$E$6:$E$15,"Víctor")+SUMIFS('S9'!$I$6:$I$15,'S9'!$B$6:$B$15,$A32,'S9'!$E$6:$E$15,"Ambos")+SUMIFS('S10'!$I$6:$I$13,'S10'!$B$6:$B$13,$A32,'S10'!$E$6:$E$13,"Víctor")+SUMIFS('S10'!$I$6:$I$13,'S10'!$B$6:$B$13,$A32,'S10'!$E$6:$E$13,"Ambos")+SUMIFS('Holgura'!$I$6:$I$11,'Holgura'!$B$6:$B$11,$A32,'Holgura'!$E$6:$E$11,"Víctor")+SUMIFS('Holgura'!$I$6:$I$11,'Holgura'!$B$6:$B$11,$A32,'Holgura'!$E$6:$E$11,"Ambos")+SUMIFS('Entrega'!$I$6:$I$9,'Entrega'!$B$6:$B$9,$A32,'Entrega'!$E$6:$E$9,"Víctor")+SUMIFS('Entrega'!$I$6:$I$9,'Entrega'!$B$6:$B$9,$A32,'Entrega'!$E$6:$E$9,"Ambos")+SUMIFS('Defensa'!$I$6:$I$10,'Defensa'!$B$6:$B$10,$A32,'Defensa'!$E$6:$E$10,"Víctor")+SUMIFS('Defensa'!$I$6:$I$10,'Defensa'!$B$6:$B$10,$A32,'Defensa'!$E$6:$E$10,"Ambos")</f>
+        <f>SUMIFS('S1'!$I$6:$I$32,'S1'!$B$6:$B$32,$A32,'S1'!$E$6:$E$32,"Víctor")+SUMIFS('S1'!$I$6:$I$32,'S1'!$B$6:$B$32,$A32,'S1'!$E$6:$E$32,"Ambos")+SUMIFS('S2'!$I$6:$I$23,'S2'!$B$6:$B$23,$A32,'S2'!$E$6:$E$23,"Víctor")+SUMIFS('S2'!$I$6:$I$23,'S2'!$B$6:$B$23,$A32,'S2'!$E$6:$E$23,"Ambos")+SUMIFS('S3'!$I$6:$I$24,'S3'!$B$6:$B$24,$A32,'S3'!$E$6:$E$24,"Víctor")+SUMIFS('S3'!$I$6:$I$24,'S3'!$B$6:$B$24,$A32,'S3'!$E$6:$E$24,"Ambos")+SUMIFS('S4'!$I$6:$I$22,'S4'!$B$6:$B$22,$A32,'S4'!$E$6:$E$22,"Víctor")+SUMIFS('S4'!$I$6:$I$22,'S4'!$B$6:$B$22,$A32,'S4'!$E$6:$E$22,"Ambos")+SUMIFS('S5'!$I$6:$I$20,'S5'!$B$6:$B$20,$A32,'S5'!$E$6:$E$20,"Víctor")+SUMIFS('S5'!$I$6:$I$20,'S5'!$B$6:$B$20,$A32,'S5'!$E$6:$E$20,"Ambos")+SUMIFS('S6'!$I$6:$I$17,'S6'!$B$6:$B$17,$A32,'S6'!$E$6:$E$17,"Víctor")+SUMIFS('S6'!$I$6:$I$17,'S6'!$B$6:$B$17,$A32,'S6'!$E$6:$E$17,"Ambos")+SUMIFS('S7'!$I$6:$I$19,'S7'!$B$6:$B$19,$A32,'S7'!$E$6:$E$19,"Víctor")+SUMIFS('S7'!$I$6:$I$19,'S7'!$B$6:$B$19,$A32,'S7'!$E$6:$E$19,"Ambos")+SUMIFS('S8'!$I$6:$I$23,'S8'!$B$6:$B$23,$A32,'S8'!$E$6:$E$23,"Víctor")+SUMIFS('S8'!$I$6:$I$23,'S8'!$B$6:$B$23,$A32,'S8'!$E$6:$E$23,"Ambos")+SUMIFS('S9'!$I$6:$I$15,'S9'!$B$6:$B$15,$A32,'S9'!$E$6:$E$15,"Víctor")+SUMIFS('S9'!$I$6:$I$15,'S9'!$B$6:$B$15,$A32,'S9'!$E$6:$E$15,"Ambos")+SUMIFS('S10'!$I$6:$I$13,'S10'!$B$6:$B$13,$A32,'S10'!$E$6:$E$13,"Víctor")+SUMIFS('S10'!$I$6:$I$13,'S10'!$B$6:$B$13,$A32,'S10'!$E$6:$E$13,"Ambos")+SUMIFS('Holgura'!$I$6:$I$11,'Holgura'!$B$6:$B$11,$A32,'Holgura'!$E$6:$E$11,"Víctor")+SUMIFS('Holgura'!$I$6:$I$11,'Holgura'!$B$6:$B$11,$A32,'Holgura'!$E$6:$E$11,"Ambos")+SUMIFS('Entrega'!$I$6:$I$9,'Entrega'!$B$6:$B$9,$A32,'Entrega'!$E$6:$E$9,"Víctor")+SUMIFS('Entrega'!$I$6:$I$9,'Entrega'!$B$6:$B$9,$A32,'Entrega'!$E$6:$E$9,"Ambos")+SUMIFS('Defensa'!$I$6:$I$10,'Defensa'!$B$6:$B$10,$A32,'Defensa'!$E$6:$E$10,"Víctor")+SUMIFS('Defensa'!$I$6:$I$10,'Defensa'!$B$6:$B$10,$A32,'Defensa'!$E$6:$E$10,"Ambos")</f>
         <v/>
       </c>
       <c r="E32" s="21">
-        <f>SUMIFS('S1'!$I$6:$I$32,'S1'!$B$6:$B$32,$A32,'S1'!$E$6:$E$32,"Diego")+SUMIFS('S1'!$I$6:$I$32,'S1'!$B$6:$B$32,$A32,'S1'!$E$6:$E$32,"Ambos")+SUMIFS('S2'!$I$6:$I$23,'S2'!$B$6:$B$23,$A32,'S2'!$E$6:$E$23,"Diego")+SUMIFS('S2'!$I$6:$I$23,'S2'!$B$6:$B$23,$A32,'S2'!$E$6:$E$23,"Ambos")+SUMIFS('S3'!$I$6:$I$19,'S3'!$B$6:$B$19,$A32,'S3'!$E$6:$E$19,"Diego")+SUMIFS('S3'!$I$6:$I$19,'S3'!$B$6:$B$19,$A32,'S3'!$E$6:$E$19,"Ambos")+SUMIFS('S4'!$I$6:$I$20,'S4'!$B$6:$B$20,$A32,'S4'!$E$6:$E$20,"Diego")+SUMIFS('S4'!$I$6:$I$20,'S4'!$B$6:$B$20,$A32,'S4'!$E$6:$E$20,"Ambos")+SUMIFS('S5'!$I$6:$I$20,'S5'!$B$6:$B$20,$A32,'S5'!$E$6:$E$20,"Diego")+SUMIFS('S5'!$I$6:$I$20,'S5'!$B$6:$B$20,$A32,'S5'!$E$6:$E$20,"Ambos")+SUMIFS('S6'!$I$6:$I$17,'S6'!$B$6:$B$17,$A32,'S6'!$E$6:$E$17,"Diego")+SUMIFS('S6'!$I$6:$I$17,'S6'!$B$6:$B$17,$A32,'S6'!$E$6:$E$17,"Ambos")+SUMIFS('S7'!$I$6:$I$19,'S7'!$B$6:$B$19,$A32,'S7'!$E$6:$E$19,"Diego")+SUMIFS('S7'!$I$6:$I$19,'S7'!$B$6:$B$19,$A32,'S7'!$E$6:$E$19,"Ambos")+SUMIFS('S8'!$I$6:$I$23,'S8'!$B$6:$B$23,$A32,'S8'!$E$6:$E$23,"Diego")+SUMIFS('S8'!$I$6:$I$23,'S8'!$B$6:$B$23,$A32,'S8'!$E$6:$E$23,"Ambos")+SUMIFS('S9'!$I$6:$I$15,'S9'!$B$6:$B$15,$A32,'S9'!$E$6:$E$15,"Diego")+SUMIFS('S9'!$I$6:$I$15,'S9'!$B$6:$B$15,$A32,'S9'!$E$6:$E$15,"Ambos")+SUMIFS('S10'!$I$6:$I$13,'S10'!$B$6:$B$13,$A32,'S10'!$E$6:$E$13,"Diego")+SUMIFS('S10'!$I$6:$I$13,'S10'!$B$6:$B$13,$A32,'S10'!$E$6:$E$13,"Ambos")+SUMIFS('Holgura'!$I$6:$I$11,'Holgura'!$B$6:$B$11,$A32,'Holgura'!$E$6:$E$11,"Diego")+SUMIFS('Holgura'!$I$6:$I$11,'Holgura'!$B$6:$B$11,$A32,'Holgura'!$E$6:$E$11,"Ambos")+SUMIFS('Entrega'!$I$6:$I$9,'Entrega'!$B$6:$B$9,$A32,'Entrega'!$E$6:$E$9,"Diego")+SUMIFS('Entrega'!$I$6:$I$9,'Entrega'!$B$6:$B$9,$A32,'Entrega'!$E$6:$E$9,"Ambos")+SUMIFS('Defensa'!$I$6:$I$10,'Defensa'!$B$6:$B$10,$A32,'Defensa'!$E$6:$E$10,"Diego")+SUMIFS('Defensa'!$I$6:$I$10,'Defensa'!$B$6:$B$10,$A32,'Defensa'!$E$6:$E$10,"Ambos")</f>
+        <f>SUMIFS('S1'!$I$6:$I$32,'S1'!$B$6:$B$32,$A32,'S1'!$E$6:$E$32,"Diego")+SUMIFS('S1'!$I$6:$I$32,'S1'!$B$6:$B$32,$A32,'S1'!$E$6:$E$32,"Ambos")+SUMIFS('S2'!$I$6:$I$23,'S2'!$B$6:$B$23,$A32,'S2'!$E$6:$E$23,"Diego")+SUMIFS('S2'!$I$6:$I$23,'S2'!$B$6:$B$23,$A32,'S2'!$E$6:$E$23,"Ambos")+SUMIFS('S3'!$I$6:$I$24,'S3'!$B$6:$B$24,$A32,'S3'!$E$6:$E$24,"Diego")+SUMIFS('S3'!$I$6:$I$24,'S3'!$B$6:$B$24,$A32,'S3'!$E$6:$E$24,"Ambos")+SUMIFS('S4'!$I$6:$I$22,'S4'!$B$6:$B$22,$A32,'S4'!$E$6:$E$22,"Diego")+SUMIFS('S4'!$I$6:$I$22,'S4'!$B$6:$B$22,$A32,'S4'!$E$6:$E$22,"Ambos")+SUMIFS('S5'!$I$6:$I$20,'S5'!$B$6:$B$20,$A32,'S5'!$E$6:$E$20,"Diego")+SUMIFS('S5'!$I$6:$I$20,'S5'!$B$6:$B$20,$A32,'S5'!$E$6:$E$20,"Ambos")+SUMIFS('S6'!$I$6:$I$17,'S6'!$B$6:$B$17,$A32,'S6'!$E$6:$E$17,"Diego")+SUMIFS('S6'!$I$6:$I$17,'S6'!$B$6:$B$17,$A32,'S6'!$E$6:$E$17,"Ambos")+SUMIFS('S7'!$I$6:$I$19,'S7'!$B$6:$B$19,$A32,'S7'!$E$6:$E$19,"Diego")+SUMIFS('S7'!$I$6:$I$19,'S7'!$B$6:$B$19,$A32,'S7'!$E$6:$E$19,"Ambos")+SUMIFS('S8'!$I$6:$I$23,'S8'!$B$6:$B$23,$A32,'S8'!$E$6:$E$23,"Diego")+SUMIFS('S8'!$I$6:$I$23,'S8'!$B$6:$B$23,$A32,'S8'!$E$6:$E$23,"Ambos")+SUMIFS('S9'!$I$6:$I$15,'S9'!$B$6:$B$15,$A32,'S9'!$E$6:$E$15,"Diego")+SUMIFS('S9'!$I$6:$I$15,'S9'!$B$6:$B$15,$A32,'S9'!$E$6:$E$15,"Ambos")+SUMIFS('S10'!$I$6:$I$13,'S10'!$B$6:$B$13,$A32,'S10'!$E$6:$E$13,"Diego")+SUMIFS('S10'!$I$6:$I$13,'S10'!$B$6:$B$13,$A32,'S10'!$E$6:$E$13,"Ambos")+SUMIFS('Holgura'!$I$6:$I$11,'Holgura'!$B$6:$B$11,$A32,'Holgura'!$E$6:$E$11,"Diego")+SUMIFS('Holgura'!$I$6:$I$11,'Holgura'!$B$6:$B$11,$A32,'Holgura'!$E$6:$E$11,"Ambos")+SUMIFS('Entrega'!$I$6:$I$9,'Entrega'!$B$6:$B$9,$A32,'Entrega'!$E$6:$E$9,"Diego")+SUMIFS('Entrega'!$I$6:$I$9,'Entrega'!$B$6:$B$9,$A32,'Entrega'!$E$6:$E$9,"Ambos")+SUMIFS('Defensa'!$I$6:$I$10,'Defensa'!$B$6:$B$10,$A32,'Defensa'!$E$6:$E$10,"Diego")+SUMIFS('Defensa'!$I$6:$I$10,'Defensa'!$B$6:$B$10,$A32,'Defensa'!$E$6:$E$10,"Ambos")</f>
         <v/>
       </c>
       <c r="F32" s="21">
-        <f>COUNTIFS('S1'!$B$6:$B$32,$A32,'S1'!$E$6:$E$32,"Víctor")+COUNTIFS('S1'!$B$6:$B$32,$A32,'S1'!$E$6:$E$32,"Ambos")+COUNTIFS('S2'!$B$6:$B$23,$A32,'S2'!$E$6:$E$23,"Víctor")+COUNTIFS('S2'!$B$6:$B$23,$A32,'S2'!$E$6:$E$23,"Ambos")+COUNTIFS('S3'!$B$6:$B$19,$A32,'S3'!$E$6:$E$19,"Víctor")+COUNTIFS('S3'!$B$6:$B$19,$A32,'S3'!$E$6:$E$19,"Ambos")+COUNTIFS('S4'!$B$6:$B$20,$A32,'S4'!$E$6:$E$20,"Víctor")+COUNTIFS('S4'!$B$6:$B$20,$A32,'S4'!$E$6:$E$20,"Ambos")+COUNTIFS('S5'!$B$6:$B$20,$A32,'S5'!$E$6:$E$20,"Víctor")+COUNTIFS('S5'!$B$6:$B$20,$A32,'S5'!$E$6:$E$20,"Ambos")+COUNTIFS('S6'!$B$6:$B$17,$A32,'S6'!$E$6:$E$17,"Víctor")+COUNTIFS('S6'!$B$6:$B$17,$A32,'S6'!$E$6:$E$17,"Ambos")+COUNTIFS('S7'!$B$6:$B$19,$A32,'S7'!$E$6:$E$19,"Víctor")+COUNTIFS('S7'!$B$6:$B$19,$A32,'S7'!$E$6:$E$19,"Ambos")+COUNTIFS('S8'!$B$6:$B$23,$A32,'S8'!$E$6:$E$23,"Víctor")+COUNTIFS('S8'!$B$6:$B$23,$A32,'S8'!$E$6:$E$23,"Ambos")+COUNTIFS('S9'!$B$6:$B$15,$A32,'S9'!$E$6:$E$15,"Víctor")+COUNTIFS('S9'!$B$6:$B$15,$A32,'S9'!$E$6:$E$15,"Ambos")+COUNTIFS('S10'!$B$6:$B$13,$A32,'S10'!$E$6:$E$13,"Víctor")+COUNTIFS('S10'!$B$6:$B$13,$A32,'S10'!$E$6:$E$13,"Ambos")+COUNTIFS('Holgura'!$B$6:$B$11,$A32,'Holgura'!$E$6:$E$11,"Víctor")+COUNTIFS('Holgura'!$B$6:$B$11,$A32,'Holgura'!$E$6:$E$11,"Ambos")+COUNTIFS('Entrega'!$B$6:$B$9,$A32,'Entrega'!$E$6:$E$9,"Víctor")+COUNTIFS('Entrega'!$B$6:$B$9,$A32,'Entrega'!$E$6:$E$9,"Ambos")+COUNTIFS('Defensa'!$B$6:$B$10,$A32,'Defensa'!$E$6:$E$10,"Víctor")+COUNTIFS('Defensa'!$B$6:$B$10,$A32,'Defensa'!$E$6:$E$10,"Ambos")</f>
+        <f>COUNTIFS('S1'!$B$6:$B$32,$A32,'S1'!$E$6:$E$32,"Víctor")+COUNTIFS('S1'!$B$6:$B$32,$A32,'S1'!$E$6:$E$32,"Ambos")+COUNTIFS('S2'!$B$6:$B$23,$A32,'S2'!$E$6:$E$23,"Víctor")+COUNTIFS('S2'!$B$6:$B$23,$A32,'S2'!$E$6:$E$23,"Ambos")+COUNTIFS('S3'!$B$6:$B$24,$A32,'S3'!$E$6:$E$24,"Víctor")+COUNTIFS('S3'!$B$6:$B$24,$A32,'S3'!$E$6:$E$24,"Ambos")+COUNTIFS('S4'!$B$6:$B$22,$A32,'S4'!$E$6:$E$22,"Víctor")+COUNTIFS('S4'!$B$6:$B$22,$A32,'S4'!$E$6:$E$22,"Ambos")+COUNTIFS('S5'!$B$6:$B$20,$A32,'S5'!$E$6:$E$20,"Víctor")+COUNTIFS('S5'!$B$6:$B$20,$A32,'S5'!$E$6:$E$20,"Ambos")+COUNTIFS('S6'!$B$6:$B$17,$A32,'S6'!$E$6:$E$17,"Víctor")+COUNTIFS('S6'!$B$6:$B$17,$A32,'S6'!$E$6:$E$17,"Ambos")+COUNTIFS('S7'!$B$6:$B$19,$A32,'S7'!$E$6:$E$19,"Víctor")+COUNTIFS('S7'!$B$6:$B$19,$A32,'S7'!$E$6:$E$19,"Ambos")+COUNTIFS('S8'!$B$6:$B$23,$A32,'S8'!$E$6:$E$23,"Víctor")+COUNTIFS('S8'!$B$6:$B$23,$A32,'S8'!$E$6:$E$23,"Ambos")+COUNTIFS('S9'!$B$6:$B$15,$A32,'S9'!$E$6:$E$15,"Víctor")+COUNTIFS('S9'!$B$6:$B$15,$A32,'S9'!$E$6:$E$15,"Ambos")+COUNTIFS('S10'!$B$6:$B$13,$A32,'S10'!$E$6:$E$13,"Víctor")+COUNTIFS('S10'!$B$6:$B$13,$A32,'S10'!$E$6:$E$13,"Ambos")+COUNTIFS('Holgura'!$B$6:$B$11,$A32,'Holgura'!$E$6:$E$11,"Víctor")+COUNTIFS('Holgura'!$B$6:$B$11,$A32,'Holgura'!$E$6:$E$11,"Ambos")+COUNTIFS('Entrega'!$B$6:$B$9,$A32,'Entrega'!$E$6:$E$9,"Víctor")+COUNTIFS('Entrega'!$B$6:$B$9,$A32,'Entrega'!$E$6:$E$9,"Ambos")+COUNTIFS('Defensa'!$B$6:$B$10,$A32,'Defensa'!$E$6:$E$10,"Víctor")+COUNTIFS('Defensa'!$B$6:$B$10,$A32,'Defensa'!$E$6:$E$10,"Ambos")</f>
         <v/>
       </c>
       <c r="G32" s="21">
-        <f>COUNTIFS('S1'!$B$6:$B$32,$A32,'S1'!$E$6:$E$32,"Diego")+COUNTIFS('S1'!$B$6:$B$32,$A32,'S1'!$E$6:$E$32,"Ambos")+COUNTIFS('S2'!$B$6:$B$23,$A32,'S2'!$E$6:$E$23,"Diego")+COUNTIFS('S2'!$B$6:$B$23,$A32,'S2'!$E$6:$E$23,"Ambos")+COUNTIFS('S3'!$B$6:$B$19,$A32,'S3'!$E$6:$E$19,"Diego")+COUNTIFS('S3'!$B$6:$B$19,$A32,'S3'!$E$6:$E$19,"Ambos")+COUNTIFS('S4'!$B$6:$B$20,$A32,'S4'!$E$6:$E$20,"Diego")+COUNTIFS('S4'!$B$6:$B$20,$A32,'S4'!$E$6:$E$20,"Ambos")+COUNTIFS('S5'!$B$6:$B$20,$A32,'S5'!$E$6:$E$20,"Diego")+COUNTIFS('S5'!$B$6:$B$20,$A32,'S5'!$E$6:$E$20,"Ambos")+COUNTIFS('S6'!$B$6:$B$17,$A32,'S6'!$E$6:$E$17,"Diego")+COUNTIFS('S6'!$B$6:$B$17,$A32,'S6'!$E$6:$E$17,"Ambos")+COUNTIFS('S7'!$B$6:$B$19,$A32,'S7'!$E$6:$E$19,"Diego")+COUNTIFS('S7'!$B$6:$B$19,$A32,'S7'!$E$6:$E$19,"Ambos")+COUNTIFS('S8'!$B$6:$B$23,$A32,'S8'!$E$6:$E$23,"Diego")+COUNTIFS('S8'!$B$6:$B$23,$A32,'S8'!$E$6:$E$23,"Ambos")+COUNTIFS('S9'!$B$6:$B$15,$A32,'S9'!$E$6:$E$15,"Diego")+COUNTIFS('S9'!$B$6:$B$15,$A32,'S9'!$E$6:$E$15,"Ambos")+COUNTIFS('S10'!$B$6:$B$13,$A32,'S10'!$E$6:$E$13,"Diego")+COUNTIFS('S10'!$B$6:$B$13,$A32,'S10'!$E$6:$E$13,"Ambos")+COUNTIFS('Holgura'!$B$6:$B$11,$A32,'Holgura'!$E$6:$E$11,"Diego")+COUNTIFS('Holgura'!$B$6:$B$11,$A32,'Holgura'!$E$6:$E$11,"Ambos")+COUNTIFS('Entrega'!$B$6:$B$9,$A32,'Entrega'!$E$6:$E$9,"Diego")+COUNTIFS('Entrega'!$B$6:$B$9,$A32,'Entrega'!$E$6:$E$9,"Ambos")+COUNTIFS('Defensa'!$B$6:$B$10,$A32,'Defensa'!$E$6:$E$10,"Diego")+COUNTIFS('Defensa'!$B$6:$B$10,$A32,'Defensa'!$E$6:$E$10,"Ambos")</f>
+        <f>COUNTIFS('S1'!$B$6:$B$32,$A32,'S1'!$E$6:$E$32,"Diego")+COUNTIFS('S1'!$B$6:$B$32,$A32,'S1'!$E$6:$E$32,"Ambos")+COUNTIFS('S2'!$B$6:$B$23,$A32,'S2'!$E$6:$E$23,"Diego")+COUNTIFS('S2'!$B$6:$B$23,$A32,'S2'!$E$6:$E$23,"Ambos")+COUNTIFS('S3'!$B$6:$B$24,$A32,'S3'!$E$6:$E$24,"Diego")+COUNTIFS('S3'!$B$6:$B$24,$A32,'S3'!$E$6:$E$24,"Ambos")+COUNTIFS('S4'!$B$6:$B$22,$A32,'S4'!$E$6:$E$22,"Diego")+COUNTIFS('S4'!$B$6:$B$22,$A32,'S4'!$E$6:$E$22,"Ambos")+COUNTIFS('S5'!$B$6:$B$20,$A32,'S5'!$E$6:$E$20,"Diego")+COUNTIFS('S5'!$B$6:$B$20,$A32,'S5'!$E$6:$E$20,"Ambos")+COUNTIFS('S6'!$B$6:$B$17,$A32,'S6'!$E$6:$E$17,"Diego")+COUNTIFS('S6'!$B$6:$B$17,$A32,'S6'!$E$6:$E$17,"Ambos")+COUNTIFS('S7'!$B$6:$B$19,$A32,'S7'!$E$6:$E$19,"Diego")+COUNTIFS('S7'!$B$6:$B$19,$A32,'S7'!$E$6:$E$19,"Ambos")+COUNTIFS('S8'!$B$6:$B$23,$A32,'S8'!$E$6:$E$23,"Diego")+COUNTIFS('S8'!$B$6:$B$23,$A32,'S8'!$E$6:$E$23,"Ambos")+COUNTIFS('S9'!$B$6:$B$15,$A32,'S9'!$E$6:$E$15,"Diego")+COUNTIFS('S9'!$B$6:$B$15,$A32,'S9'!$E$6:$E$15,"Ambos")+COUNTIFS('S10'!$B$6:$B$13,$A32,'S10'!$E$6:$E$13,"Diego")+COUNTIFS('S10'!$B$6:$B$13,$A32,'S10'!$E$6:$E$13,"Ambos")+COUNTIFS('Holgura'!$B$6:$B$11,$A32,'Holgura'!$E$6:$E$11,"Diego")+COUNTIFS('Holgura'!$B$6:$B$11,$A32,'Holgura'!$E$6:$E$11,"Ambos")+COUNTIFS('Entrega'!$B$6:$B$9,$A32,'Entrega'!$E$6:$E$9,"Diego")+COUNTIFS('Entrega'!$B$6:$B$9,$A32,'Entrega'!$E$6:$E$9,"Ambos")+COUNTIFS('Defensa'!$B$6:$B$10,$A32,'Defensa'!$E$6:$E$10,"Diego")+COUNTIFS('Defensa'!$B$6:$B$10,$A32,'Defensa'!$E$6:$E$10,"Ambos")</f>
         <v/>
       </c>
     </row>
@@ -9492,19 +9513,19 @@
         <v/>
       </c>
       <c r="D33" s="21">
-        <f>SUMIFS('S1'!$I$6:$I$32,'S1'!$B$6:$B$32,$A33,'S1'!$E$6:$E$32,"Víctor")+SUMIFS('S1'!$I$6:$I$32,'S1'!$B$6:$B$32,$A33,'S1'!$E$6:$E$32,"Ambos")+SUMIFS('S2'!$I$6:$I$23,'S2'!$B$6:$B$23,$A33,'S2'!$E$6:$E$23,"Víctor")+SUMIFS('S2'!$I$6:$I$23,'S2'!$B$6:$B$23,$A33,'S2'!$E$6:$E$23,"Ambos")+SUMIFS('S3'!$I$6:$I$19,'S3'!$B$6:$B$19,$A33,'S3'!$E$6:$E$19,"Víctor")+SUMIFS('S3'!$I$6:$I$19,'S3'!$B$6:$B$19,$A33,'S3'!$E$6:$E$19,"Ambos")+SUMIFS('S4'!$I$6:$I$20,'S4'!$B$6:$B$20,$A33,'S4'!$E$6:$E$20,"Víctor")+SUMIFS('S4'!$I$6:$I$20,'S4'!$B$6:$B$20,$A33,'S4'!$E$6:$E$20,"Ambos")+SUMIFS('S5'!$I$6:$I$20,'S5'!$B$6:$B$20,$A33,'S5'!$E$6:$E$20,"Víctor")+SUMIFS('S5'!$I$6:$I$20,'S5'!$B$6:$B$20,$A33,'S5'!$E$6:$E$20,"Ambos")+SUMIFS('S6'!$I$6:$I$17,'S6'!$B$6:$B$17,$A33,'S6'!$E$6:$E$17,"Víctor")+SUMIFS('S6'!$I$6:$I$17,'S6'!$B$6:$B$17,$A33,'S6'!$E$6:$E$17,"Ambos")+SUMIFS('S7'!$I$6:$I$19,'S7'!$B$6:$B$19,$A33,'S7'!$E$6:$E$19,"Víctor")+SUMIFS('S7'!$I$6:$I$19,'S7'!$B$6:$B$19,$A33,'S7'!$E$6:$E$19,"Ambos")+SUMIFS('S8'!$I$6:$I$23,'S8'!$B$6:$B$23,$A33,'S8'!$E$6:$E$23,"Víctor")+SUMIFS('S8'!$I$6:$I$23,'S8'!$B$6:$B$23,$A33,'S8'!$E$6:$E$23,"Ambos")+SUMIFS('S9'!$I$6:$I$15,'S9'!$B$6:$B$15,$A33,'S9'!$E$6:$E$15,"Víctor")+SUMIFS('S9'!$I$6:$I$15,'S9'!$B$6:$B$15,$A33,'S9'!$E$6:$E$15,"Ambos")+SUMIFS('S10'!$I$6:$I$13,'S10'!$B$6:$B$13,$A33,'S10'!$E$6:$E$13,"Víctor")+SUMIFS('S10'!$I$6:$I$13,'S10'!$B$6:$B$13,$A33,'S10'!$E$6:$E$13,"Ambos")+SUMIFS('Holgura'!$I$6:$I$11,'Holgura'!$B$6:$B$11,$A33,'Holgura'!$E$6:$E$11,"Víctor")+SUMIFS('Holgura'!$I$6:$I$11,'Holgura'!$B$6:$B$11,$A33,'Holgura'!$E$6:$E$11,"Ambos")+SUMIFS('Entrega'!$I$6:$I$9,'Entrega'!$B$6:$B$9,$A33,'Entrega'!$E$6:$E$9,"Víctor")+SUMIFS('Entrega'!$I$6:$I$9,'Entrega'!$B$6:$B$9,$A33,'Entrega'!$E$6:$E$9,"Ambos")+SUMIFS('Defensa'!$I$6:$I$10,'Defensa'!$B$6:$B$10,$A33,'Defensa'!$E$6:$E$10,"Víctor")+SUMIFS('Defensa'!$I$6:$I$10,'Defensa'!$B$6:$B$10,$A33,'Defensa'!$E$6:$E$10,"Ambos")</f>
+        <f>SUMIFS('S1'!$I$6:$I$32,'S1'!$B$6:$B$32,$A33,'S1'!$E$6:$E$32,"Víctor")+SUMIFS('S1'!$I$6:$I$32,'S1'!$B$6:$B$32,$A33,'S1'!$E$6:$E$32,"Ambos")+SUMIFS('S2'!$I$6:$I$23,'S2'!$B$6:$B$23,$A33,'S2'!$E$6:$E$23,"Víctor")+SUMIFS('S2'!$I$6:$I$23,'S2'!$B$6:$B$23,$A33,'S2'!$E$6:$E$23,"Ambos")+SUMIFS('S3'!$I$6:$I$24,'S3'!$B$6:$B$24,$A33,'S3'!$E$6:$E$24,"Víctor")+SUMIFS('S3'!$I$6:$I$24,'S3'!$B$6:$B$24,$A33,'S3'!$E$6:$E$24,"Ambos")+SUMIFS('S4'!$I$6:$I$22,'S4'!$B$6:$B$22,$A33,'S4'!$E$6:$E$22,"Víctor")+SUMIFS('S4'!$I$6:$I$22,'S4'!$B$6:$B$22,$A33,'S4'!$E$6:$E$22,"Ambos")+SUMIFS('S5'!$I$6:$I$20,'S5'!$B$6:$B$20,$A33,'S5'!$E$6:$E$20,"Víctor")+SUMIFS('S5'!$I$6:$I$20,'S5'!$B$6:$B$20,$A33,'S5'!$E$6:$E$20,"Ambos")+SUMIFS('S6'!$I$6:$I$17,'S6'!$B$6:$B$17,$A33,'S6'!$E$6:$E$17,"Víctor")+SUMIFS('S6'!$I$6:$I$17,'S6'!$B$6:$B$17,$A33,'S6'!$E$6:$E$17,"Ambos")+SUMIFS('S7'!$I$6:$I$19,'S7'!$B$6:$B$19,$A33,'S7'!$E$6:$E$19,"Víctor")+SUMIFS('S7'!$I$6:$I$19,'S7'!$B$6:$B$19,$A33,'S7'!$E$6:$E$19,"Ambos")+SUMIFS('S8'!$I$6:$I$23,'S8'!$B$6:$B$23,$A33,'S8'!$E$6:$E$23,"Víctor")+SUMIFS('S8'!$I$6:$I$23,'S8'!$B$6:$B$23,$A33,'S8'!$E$6:$E$23,"Ambos")+SUMIFS('S9'!$I$6:$I$15,'S9'!$B$6:$B$15,$A33,'S9'!$E$6:$E$15,"Víctor")+SUMIFS('S9'!$I$6:$I$15,'S9'!$B$6:$B$15,$A33,'S9'!$E$6:$E$15,"Ambos")+SUMIFS('S10'!$I$6:$I$13,'S10'!$B$6:$B$13,$A33,'S10'!$E$6:$E$13,"Víctor")+SUMIFS('S10'!$I$6:$I$13,'S10'!$B$6:$B$13,$A33,'S10'!$E$6:$E$13,"Ambos")+SUMIFS('Holgura'!$I$6:$I$11,'Holgura'!$B$6:$B$11,$A33,'Holgura'!$E$6:$E$11,"Víctor")+SUMIFS('Holgura'!$I$6:$I$11,'Holgura'!$B$6:$B$11,$A33,'Holgura'!$E$6:$E$11,"Ambos")+SUMIFS('Entrega'!$I$6:$I$9,'Entrega'!$B$6:$B$9,$A33,'Entrega'!$E$6:$E$9,"Víctor")+SUMIFS('Entrega'!$I$6:$I$9,'Entrega'!$B$6:$B$9,$A33,'Entrega'!$E$6:$E$9,"Ambos")+SUMIFS('Defensa'!$I$6:$I$10,'Defensa'!$B$6:$B$10,$A33,'Defensa'!$E$6:$E$10,"Víctor")+SUMIFS('Defensa'!$I$6:$I$10,'Defensa'!$B$6:$B$10,$A33,'Defensa'!$E$6:$E$10,"Ambos")</f>
         <v/>
       </c>
       <c r="E33" s="21">
-        <f>SUMIFS('S1'!$I$6:$I$32,'S1'!$B$6:$B$32,$A33,'S1'!$E$6:$E$32,"Diego")+SUMIFS('S1'!$I$6:$I$32,'S1'!$B$6:$B$32,$A33,'S1'!$E$6:$E$32,"Ambos")+SUMIFS('S2'!$I$6:$I$23,'S2'!$B$6:$B$23,$A33,'S2'!$E$6:$E$23,"Diego")+SUMIFS('S2'!$I$6:$I$23,'S2'!$B$6:$B$23,$A33,'S2'!$E$6:$E$23,"Ambos")+SUMIFS('S3'!$I$6:$I$19,'S3'!$B$6:$B$19,$A33,'S3'!$E$6:$E$19,"Diego")+SUMIFS('S3'!$I$6:$I$19,'S3'!$B$6:$B$19,$A33,'S3'!$E$6:$E$19,"Ambos")+SUMIFS('S4'!$I$6:$I$20,'S4'!$B$6:$B$20,$A33,'S4'!$E$6:$E$20,"Diego")+SUMIFS('S4'!$I$6:$I$20,'S4'!$B$6:$B$20,$A33,'S4'!$E$6:$E$20,"Ambos")+SUMIFS('S5'!$I$6:$I$20,'S5'!$B$6:$B$20,$A33,'S5'!$E$6:$E$20,"Diego")+SUMIFS('S5'!$I$6:$I$20,'S5'!$B$6:$B$20,$A33,'S5'!$E$6:$E$20,"Ambos")+SUMIFS('S6'!$I$6:$I$17,'S6'!$B$6:$B$17,$A33,'S6'!$E$6:$E$17,"Diego")+SUMIFS('S6'!$I$6:$I$17,'S6'!$B$6:$B$17,$A33,'S6'!$E$6:$E$17,"Ambos")+SUMIFS('S7'!$I$6:$I$19,'S7'!$B$6:$B$19,$A33,'S7'!$E$6:$E$19,"Diego")+SUMIFS('S7'!$I$6:$I$19,'S7'!$B$6:$B$19,$A33,'S7'!$E$6:$E$19,"Ambos")+SUMIFS('S8'!$I$6:$I$23,'S8'!$B$6:$B$23,$A33,'S8'!$E$6:$E$23,"Diego")+SUMIFS('S8'!$I$6:$I$23,'S8'!$B$6:$B$23,$A33,'S8'!$E$6:$E$23,"Ambos")+SUMIFS('S9'!$I$6:$I$15,'S9'!$B$6:$B$15,$A33,'S9'!$E$6:$E$15,"Diego")+SUMIFS('S9'!$I$6:$I$15,'S9'!$B$6:$B$15,$A33,'S9'!$E$6:$E$15,"Ambos")+SUMIFS('S10'!$I$6:$I$13,'S10'!$B$6:$B$13,$A33,'S10'!$E$6:$E$13,"Diego")+SUMIFS('S10'!$I$6:$I$13,'S10'!$B$6:$B$13,$A33,'S10'!$E$6:$E$13,"Ambos")+SUMIFS('Holgura'!$I$6:$I$11,'Holgura'!$B$6:$B$11,$A33,'Holgura'!$E$6:$E$11,"Diego")+SUMIFS('Holgura'!$I$6:$I$11,'Holgura'!$B$6:$B$11,$A33,'Holgura'!$E$6:$E$11,"Ambos")+SUMIFS('Entrega'!$I$6:$I$9,'Entrega'!$B$6:$B$9,$A33,'Entrega'!$E$6:$E$9,"Diego")+SUMIFS('Entrega'!$I$6:$I$9,'Entrega'!$B$6:$B$9,$A33,'Entrega'!$E$6:$E$9,"Ambos")+SUMIFS('Defensa'!$I$6:$I$10,'Defensa'!$B$6:$B$10,$A33,'Defensa'!$E$6:$E$10,"Diego")+SUMIFS('Defensa'!$I$6:$I$10,'Defensa'!$B$6:$B$10,$A33,'Defensa'!$E$6:$E$10,"Ambos")</f>
+        <f>SUMIFS('S1'!$I$6:$I$32,'S1'!$B$6:$B$32,$A33,'S1'!$E$6:$E$32,"Diego")+SUMIFS('S1'!$I$6:$I$32,'S1'!$B$6:$B$32,$A33,'S1'!$E$6:$E$32,"Ambos")+SUMIFS('S2'!$I$6:$I$23,'S2'!$B$6:$B$23,$A33,'S2'!$E$6:$E$23,"Diego")+SUMIFS('S2'!$I$6:$I$23,'S2'!$B$6:$B$23,$A33,'S2'!$E$6:$E$23,"Ambos")+SUMIFS('S3'!$I$6:$I$24,'S3'!$B$6:$B$24,$A33,'S3'!$E$6:$E$24,"Diego")+SUMIFS('S3'!$I$6:$I$24,'S3'!$B$6:$B$24,$A33,'S3'!$E$6:$E$24,"Ambos")+SUMIFS('S4'!$I$6:$I$22,'S4'!$B$6:$B$22,$A33,'S4'!$E$6:$E$22,"Diego")+SUMIFS('S4'!$I$6:$I$22,'S4'!$B$6:$B$22,$A33,'S4'!$E$6:$E$22,"Ambos")+SUMIFS('S5'!$I$6:$I$20,'S5'!$B$6:$B$20,$A33,'S5'!$E$6:$E$20,"Diego")+SUMIFS('S5'!$I$6:$I$20,'S5'!$B$6:$B$20,$A33,'S5'!$E$6:$E$20,"Ambos")+SUMIFS('S6'!$I$6:$I$17,'S6'!$B$6:$B$17,$A33,'S6'!$E$6:$E$17,"Diego")+SUMIFS('S6'!$I$6:$I$17,'S6'!$B$6:$B$17,$A33,'S6'!$E$6:$E$17,"Ambos")+SUMIFS('S7'!$I$6:$I$19,'S7'!$B$6:$B$19,$A33,'S7'!$E$6:$E$19,"Diego")+SUMIFS('S7'!$I$6:$I$19,'S7'!$B$6:$B$19,$A33,'S7'!$E$6:$E$19,"Ambos")+SUMIFS('S8'!$I$6:$I$23,'S8'!$B$6:$B$23,$A33,'S8'!$E$6:$E$23,"Diego")+SUMIFS('S8'!$I$6:$I$23,'S8'!$B$6:$B$23,$A33,'S8'!$E$6:$E$23,"Ambos")+SUMIFS('S9'!$I$6:$I$15,'S9'!$B$6:$B$15,$A33,'S9'!$E$6:$E$15,"Diego")+SUMIFS('S9'!$I$6:$I$15,'S9'!$B$6:$B$15,$A33,'S9'!$E$6:$E$15,"Ambos")+SUMIFS('S10'!$I$6:$I$13,'S10'!$B$6:$B$13,$A33,'S10'!$E$6:$E$13,"Diego")+SUMIFS('S10'!$I$6:$I$13,'S10'!$B$6:$B$13,$A33,'S10'!$E$6:$E$13,"Ambos")+SUMIFS('Holgura'!$I$6:$I$11,'Holgura'!$B$6:$B$11,$A33,'Holgura'!$E$6:$E$11,"Diego")+SUMIFS('Holgura'!$I$6:$I$11,'Holgura'!$B$6:$B$11,$A33,'Holgura'!$E$6:$E$11,"Ambos")+SUMIFS('Entrega'!$I$6:$I$9,'Entrega'!$B$6:$B$9,$A33,'Entrega'!$E$6:$E$9,"Diego")+SUMIFS('Entrega'!$I$6:$I$9,'Entrega'!$B$6:$B$9,$A33,'Entrega'!$E$6:$E$9,"Ambos")+SUMIFS('Defensa'!$I$6:$I$10,'Defensa'!$B$6:$B$10,$A33,'Defensa'!$E$6:$E$10,"Diego")+SUMIFS('Defensa'!$I$6:$I$10,'Defensa'!$B$6:$B$10,$A33,'Defensa'!$E$6:$E$10,"Ambos")</f>
         <v/>
       </c>
       <c r="F33" s="21">
-        <f>COUNTIFS('S1'!$B$6:$B$32,$A33,'S1'!$E$6:$E$32,"Víctor")+COUNTIFS('S1'!$B$6:$B$32,$A33,'S1'!$E$6:$E$32,"Ambos")+COUNTIFS('S2'!$B$6:$B$23,$A33,'S2'!$E$6:$E$23,"Víctor")+COUNTIFS('S2'!$B$6:$B$23,$A33,'S2'!$E$6:$E$23,"Ambos")+COUNTIFS('S3'!$B$6:$B$19,$A33,'S3'!$E$6:$E$19,"Víctor")+COUNTIFS('S3'!$B$6:$B$19,$A33,'S3'!$E$6:$E$19,"Ambos")+COUNTIFS('S4'!$B$6:$B$20,$A33,'S4'!$E$6:$E$20,"Víctor")+COUNTIFS('S4'!$B$6:$B$20,$A33,'S4'!$E$6:$E$20,"Ambos")+COUNTIFS('S5'!$B$6:$B$20,$A33,'S5'!$E$6:$E$20,"Víctor")+COUNTIFS('S5'!$B$6:$B$20,$A33,'S5'!$E$6:$E$20,"Ambos")+COUNTIFS('S6'!$B$6:$B$17,$A33,'S6'!$E$6:$E$17,"Víctor")+COUNTIFS('S6'!$B$6:$B$17,$A33,'S6'!$E$6:$E$17,"Ambos")+COUNTIFS('S7'!$B$6:$B$19,$A33,'S7'!$E$6:$E$19,"Víctor")+COUNTIFS('S7'!$B$6:$B$19,$A33,'S7'!$E$6:$E$19,"Ambos")+COUNTIFS('S8'!$B$6:$B$23,$A33,'S8'!$E$6:$E$23,"Víctor")+COUNTIFS('S8'!$B$6:$B$23,$A33,'S8'!$E$6:$E$23,"Ambos")+COUNTIFS('S9'!$B$6:$B$15,$A33,'S9'!$E$6:$E$15,"Víctor")+COUNTIFS('S9'!$B$6:$B$15,$A33,'S9'!$E$6:$E$15,"Ambos")+COUNTIFS('S10'!$B$6:$B$13,$A33,'S10'!$E$6:$E$13,"Víctor")+COUNTIFS('S10'!$B$6:$B$13,$A33,'S10'!$E$6:$E$13,"Ambos")+COUNTIFS('Holgura'!$B$6:$B$11,$A33,'Holgura'!$E$6:$E$11,"Víctor")+COUNTIFS('Holgura'!$B$6:$B$11,$A33,'Holgura'!$E$6:$E$11,"Ambos")+COUNTIFS('Entrega'!$B$6:$B$9,$A33,'Entrega'!$E$6:$E$9,"Víctor")+COUNTIFS('Entrega'!$B$6:$B$9,$A33,'Entrega'!$E$6:$E$9,"Ambos")+COUNTIFS('Defensa'!$B$6:$B$10,$A33,'Defensa'!$E$6:$E$10,"Víctor")+COUNTIFS('Defensa'!$B$6:$B$10,$A33,'Defensa'!$E$6:$E$10,"Ambos")</f>
+        <f>COUNTIFS('S1'!$B$6:$B$32,$A33,'S1'!$E$6:$E$32,"Víctor")+COUNTIFS('S1'!$B$6:$B$32,$A33,'S1'!$E$6:$E$32,"Ambos")+COUNTIFS('S2'!$B$6:$B$23,$A33,'S2'!$E$6:$E$23,"Víctor")+COUNTIFS('S2'!$B$6:$B$23,$A33,'S2'!$E$6:$E$23,"Ambos")+COUNTIFS('S3'!$B$6:$B$24,$A33,'S3'!$E$6:$E$24,"Víctor")+COUNTIFS('S3'!$B$6:$B$24,$A33,'S3'!$E$6:$E$24,"Ambos")+COUNTIFS('S4'!$B$6:$B$22,$A33,'S4'!$E$6:$E$22,"Víctor")+COUNTIFS('S4'!$B$6:$B$22,$A33,'S4'!$E$6:$E$22,"Ambos")+COUNTIFS('S5'!$B$6:$B$20,$A33,'S5'!$E$6:$E$20,"Víctor")+COUNTIFS('S5'!$B$6:$B$20,$A33,'S5'!$E$6:$E$20,"Ambos")+COUNTIFS('S6'!$B$6:$B$17,$A33,'S6'!$E$6:$E$17,"Víctor")+COUNTIFS('S6'!$B$6:$B$17,$A33,'S6'!$E$6:$E$17,"Ambos")+COUNTIFS('S7'!$B$6:$B$19,$A33,'S7'!$E$6:$E$19,"Víctor")+COUNTIFS('S7'!$B$6:$B$19,$A33,'S7'!$E$6:$E$19,"Ambos")+COUNTIFS('S8'!$B$6:$B$23,$A33,'S8'!$E$6:$E$23,"Víctor")+COUNTIFS('S8'!$B$6:$B$23,$A33,'S8'!$E$6:$E$23,"Ambos")+COUNTIFS('S9'!$B$6:$B$15,$A33,'S9'!$E$6:$E$15,"Víctor")+COUNTIFS('S9'!$B$6:$B$15,$A33,'S9'!$E$6:$E$15,"Ambos")+COUNTIFS('S10'!$B$6:$B$13,$A33,'S10'!$E$6:$E$13,"Víctor")+COUNTIFS('S10'!$B$6:$B$13,$A33,'S10'!$E$6:$E$13,"Ambos")+COUNTIFS('Holgura'!$B$6:$B$11,$A33,'Holgura'!$E$6:$E$11,"Víctor")+COUNTIFS('Holgura'!$B$6:$B$11,$A33,'Holgura'!$E$6:$E$11,"Ambos")+COUNTIFS('Entrega'!$B$6:$B$9,$A33,'Entrega'!$E$6:$E$9,"Víctor")+COUNTIFS('Entrega'!$B$6:$B$9,$A33,'Entrega'!$E$6:$E$9,"Ambos")+COUNTIFS('Defensa'!$B$6:$B$10,$A33,'Defensa'!$E$6:$E$10,"Víctor")+COUNTIFS('Defensa'!$B$6:$B$10,$A33,'Defensa'!$E$6:$E$10,"Ambos")</f>
         <v/>
       </c>
       <c r="G33" s="21">
-        <f>COUNTIFS('S1'!$B$6:$B$32,$A33,'S1'!$E$6:$E$32,"Diego")+COUNTIFS('S1'!$B$6:$B$32,$A33,'S1'!$E$6:$E$32,"Ambos")+COUNTIFS('S2'!$B$6:$B$23,$A33,'S2'!$E$6:$E$23,"Diego")+COUNTIFS('S2'!$B$6:$B$23,$A33,'S2'!$E$6:$E$23,"Ambos")+COUNTIFS('S3'!$B$6:$B$19,$A33,'S3'!$E$6:$E$19,"Diego")+COUNTIFS('S3'!$B$6:$B$19,$A33,'S3'!$E$6:$E$19,"Ambos")+COUNTIFS('S4'!$B$6:$B$20,$A33,'S4'!$E$6:$E$20,"Diego")+COUNTIFS('S4'!$B$6:$B$20,$A33,'S4'!$E$6:$E$20,"Ambos")+COUNTIFS('S5'!$B$6:$B$20,$A33,'S5'!$E$6:$E$20,"Diego")+COUNTIFS('S5'!$B$6:$B$20,$A33,'S5'!$E$6:$E$20,"Ambos")+COUNTIFS('S6'!$B$6:$B$17,$A33,'S6'!$E$6:$E$17,"Diego")+COUNTIFS('S6'!$B$6:$B$17,$A33,'S6'!$E$6:$E$17,"Ambos")+COUNTIFS('S7'!$B$6:$B$19,$A33,'S7'!$E$6:$E$19,"Diego")+COUNTIFS('S7'!$B$6:$B$19,$A33,'S7'!$E$6:$E$19,"Ambos")+COUNTIFS('S8'!$B$6:$B$23,$A33,'S8'!$E$6:$E$23,"Diego")+COUNTIFS('S8'!$B$6:$B$23,$A33,'S8'!$E$6:$E$23,"Ambos")+COUNTIFS('S9'!$B$6:$B$15,$A33,'S9'!$E$6:$E$15,"Diego")+COUNTIFS('S9'!$B$6:$B$15,$A33,'S9'!$E$6:$E$15,"Ambos")+COUNTIFS('S10'!$B$6:$B$13,$A33,'S10'!$E$6:$E$13,"Diego")+COUNTIFS('S10'!$B$6:$B$13,$A33,'S10'!$E$6:$E$13,"Ambos")+COUNTIFS('Holgura'!$B$6:$B$11,$A33,'Holgura'!$E$6:$E$11,"Diego")+COUNTIFS('Holgura'!$B$6:$B$11,$A33,'Holgura'!$E$6:$E$11,"Ambos")+COUNTIFS('Entrega'!$B$6:$B$9,$A33,'Entrega'!$E$6:$E$9,"Diego")+COUNTIFS('Entrega'!$B$6:$B$9,$A33,'Entrega'!$E$6:$E$9,"Ambos")+COUNTIFS('Defensa'!$B$6:$B$10,$A33,'Defensa'!$E$6:$E$10,"Diego")+COUNTIFS('Defensa'!$B$6:$B$10,$A33,'Defensa'!$E$6:$E$10,"Ambos")</f>
+        <f>COUNTIFS('S1'!$B$6:$B$32,$A33,'S1'!$E$6:$E$32,"Diego")+COUNTIFS('S1'!$B$6:$B$32,$A33,'S1'!$E$6:$E$32,"Ambos")+COUNTIFS('S2'!$B$6:$B$23,$A33,'S2'!$E$6:$E$23,"Diego")+COUNTIFS('S2'!$B$6:$B$23,$A33,'S2'!$E$6:$E$23,"Ambos")+COUNTIFS('S3'!$B$6:$B$24,$A33,'S3'!$E$6:$E$24,"Diego")+COUNTIFS('S3'!$B$6:$B$24,$A33,'S3'!$E$6:$E$24,"Ambos")+COUNTIFS('S4'!$B$6:$B$22,$A33,'S4'!$E$6:$E$22,"Diego")+COUNTIFS('S4'!$B$6:$B$22,$A33,'S4'!$E$6:$E$22,"Ambos")+COUNTIFS('S5'!$B$6:$B$20,$A33,'S5'!$E$6:$E$20,"Diego")+COUNTIFS('S5'!$B$6:$B$20,$A33,'S5'!$E$6:$E$20,"Ambos")+COUNTIFS('S6'!$B$6:$B$17,$A33,'S6'!$E$6:$E$17,"Diego")+COUNTIFS('S6'!$B$6:$B$17,$A33,'S6'!$E$6:$E$17,"Ambos")+COUNTIFS('S7'!$B$6:$B$19,$A33,'S7'!$E$6:$E$19,"Diego")+COUNTIFS('S7'!$B$6:$B$19,$A33,'S7'!$E$6:$E$19,"Ambos")+COUNTIFS('S8'!$B$6:$B$23,$A33,'S8'!$E$6:$E$23,"Diego")+COUNTIFS('S8'!$B$6:$B$23,$A33,'S8'!$E$6:$E$23,"Ambos")+COUNTIFS('S9'!$B$6:$B$15,$A33,'S9'!$E$6:$E$15,"Diego")+COUNTIFS('S9'!$B$6:$B$15,$A33,'S9'!$E$6:$E$15,"Ambos")+COUNTIFS('S10'!$B$6:$B$13,$A33,'S10'!$E$6:$E$13,"Diego")+COUNTIFS('S10'!$B$6:$B$13,$A33,'S10'!$E$6:$E$13,"Ambos")+COUNTIFS('Holgura'!$B$6:$B$11,$A33,'Holgura'!$E$6:$E$11,"Diego")+COUNTIFS('Holgura'!$B$6:$B$11,$A33,'Holgura'!$E$6:$E$11,"Ambos")+COUNTIFS('Entrega'!$B$6:$B$9,$A33,'Entrega'!$E$6:$E$9,"Diego")+COUNTIFS('Entrega'!$B$6:$B$9,$A33,'Entrega'!$E$6:$E$9,"Ambos")+COUNTIFS('Defensa'!$B$6:$B$10,$A33,'Defensa'!$E$6:$E$10,"Diego")+COUNTIFS('Defensa'!$B$6:$B$10,$A33,'Defensa'!$E$6:$E$10,"Ambos")</f>
         <v/>
       </c>
     </row>
@@ -9521,19 +9542,19 @@
         <v/>
       </c>
       <c r="D34" s="21">
-        <f>SUMIFS('S1'!$I$6:$I$32,'S1'!$B$6:$B$32,$A34,'S1'!$E$6:$E$32,"Víctor")+SUMIFS('S1'!$I$6:$I$32,'S1'!$B$6:$B$32,$A34,'S1'!$E$6:$E$32,"Ambos")+SUMIFS('S2'!$I$6:$I$23,'S2'!$B$6:$B$23,$A34,'S2'!$E$6:$E$23,"Víctor")+SUMIFS('S2'!$I$6:$I$23,'S2'!$B$6:$B$23,$A34,'S2'!$E$6:$E$23,"Ambos")+SUMIFS('S3'!$I$6:$I$19,'S3'!$B$6:$B$19,$A34,'S3'!$E$6:$E$19,"Víctor")+SUMIFS('S3'!$I$6:$I$19,'S3'!$B$6:$B$19,$A34,'S3'!$E$6:$E$19,"Ambos")+SUMIFS('S4'!$I$6:$I$20,'S4'!$B$6:$B$20,$A34,'S4'!$E$6:$E$20,"Víctor")+SUMIFS('S4'!$I$6:$I$20,'S4'!$B$6:$B$20,$A34,'S4'!$E$6:$E$20,"Ambos")+SUMIFS('S5'!$I$6:$I$20,'S5'!$B$6:$B$20,$A34,'S5'!$E$6:$E$20,"Víctor")+SUMIFS('S5'!$I$6:$I$20,'S5'!$B$6:$B$20,$A34,'S5'!$E$6:$E$20,"Ambos")+SUMIFS('S6'!$I$6:$I$17,'S6'!$B$6:$B$17,$A34,'S6'!$E$6:$E$17,"Víctor")+SUMIFS('S6'!$I$6:$I$17,'S6'!$B$6:$B$17,$A34,'S6'!$E$6:$E$17,"Ambos")+SUMIFS('S7'!$I$6:$I$19,'S7'!$B$6:$B$19,$A34,'S7'!$E$6:$E$19,"Víctor")+SUMIFS('S7'!$I$6:$I$19,'S7'!$B$6:$B$19,$A34,'S7'!$E$6:$E$19,"Ambos")+SUMIFS('S8'!$I$6:$I$23,'S8'!$B$6:$B$23,$A34,'S8'!$E$6:$E$23,"Víctor")+SUMIFS('S8'!$I$6:$I$23,'S8'!$B$6:$B$23,$A34,'S8'!$E$6:$E$23,"Ambos")+SUMIFS('S9'!$I$6:$I$15,'S9'!$B$6:$B$15,$A34,'S9'!$E$6:$E$15,"Víctor")+SUMIFS('S9'!$I$6:$I$15,'S9'!$B$6:$B$15,$A34,'S9'!$E$6:$E$15,"Ambos")+SUMIFS('S10'!$I$6:$I$13,'S10'!$B$6:$B$13,$A34,'S10'!$E$6:$E$13,"Víctor")+SUMIFS('S10'!$I$6:$I$13,'S10'!$B$6:$B$13,$A34,'S10'!$E$6:$E$13,"Ambos")+SUMIFS('Holgura'!$I$6:$I$11,'Holgura'!$B$6:$B$11,$A34,'Holgura'!$E$6:$E$11,"Víctor")+SUMIFS('Holgura'!$I$6:$I$11,'Holgura'!$B$6:$B$11,$A34,'Holgura'!$E$6:$E$11,"Ambos")+SUMIFS('Entrega'!$I$6:$I$9,'Entrega'!$B$6:$B$9,$A34,'Entrega'!$E$6:$E$9,"Víctor")+SUMIFS('Entrega'!$I$6:$I$9,'Entrega'!$B$6:$B$9,$A34,'Entrega'!$E$6:$E$9,"Ambos")+SUMIFS('Defensa'!$I$6:$I$10,'Defensa'!$B$6:$B$10,$A34,'Defensa'!$E$6:$E$10,"Víctor")+SUMIFS('Defensa'!$I$6:$I$10,'Defensa'!$B$6:$B$10,$A34,'Defensa'!$E$6:$E$10,"Ambos")</f>
+        <f>SUMIFS('S1'!$I$6:$I$32,'S1'!$B$6:$B$32,$A34,'S1'!$E$6:$E$32,"Víctor")+SUMIFS('S1'!$I$6:$I$32,'S1'!$B$6:$B$32,$A34,'S1'!$E$6:$E$32,"Ambos")+SUMIFS('S2'!$I$6:$I$23,'S2'!$B$6:$B$23,$A34,'S2'!$E$6:$E$23,"Víctor")+SUMIFS('S2'!$I$6:$I$23,'S2'!$B$6:$B$23,$A34,'S2'!$E$6:$E$23,"Ambos")+SUMIFS('S3'!$I$6:$I$24,'S3'!$B$6:$B$24,$A34,'S3'!$E$6:$E$24,"Víctor")+SUMIFS('S3'!$I$6:$I$24,'S3'!$B$6:$B$24,$A34,'S3'!$E$6:$E$24,"Ambos")+SUMIFS('S4'!$I$6:$I$22,'S4'!$B$6:$B$22,$A34,'S4'!$E$6:$E$22,"Víctor")+SUMIFS('S4'!$I$6:$I$22,'S4'!$B$6:$B$22,$A34,'S4'!$E$6:$E$22,"Ambos")+SUMIFS('S5'!$I$6:$I$20,'S5'!$B$6:$B$20,$A34,'S5'!$E$6:$E$20,"Víctor")+SUMIFS('S5'!$I$6:$I$20,'S5'!$B$6:$B$20,$A34,'S5'!$E$6:$E$20,"Ambos")+SUMIFS('S6'!$I$6:$I$17,'S6'!$B$6:$B$17,$A34,'S6'!$E$6:$E$17,"Víctor")+SUMIFS('S6'!$I$6:$I$17,'S6'!$B$6:$B$17,$A34,'S6'!$E$6:$E$17,"Ambos")+SUMIFS('S7'!$I$6:$I$19,'S7'!$B$6:$B$19,$A34,'S7'!$E$6:$E$19,"Víctor")+SUMIFS('S7'!$I$6:$I$19,'S7'!$B$6:$B$19,$A34,'S7'!$E$6:$E$19,"Ambos")+SUMIFS('S8'!$I$6:$I$23,'S8'!$B$6:$B$23,$A34,'S8'!$E$6:$E$23,"Víctor")+SUMIFS('S8'!$I$6:$I$23,'S8'!$B$6:$B$23,$A34,'S8'!$E$6:$E$23,"Ambos")+SUMIFS('S9'!$I$6:$I$15,'S9'!$B$6:$B$15,$A34,'S9'!$E$6:$E$15,"Víctor")+SUMIFS('S9'!$I$6:$I$15,'S9'!$B$6:$B$15,$A34,'S9'!$E$6:$E$15,"Ambos")+SUMIFS('S10'!$I$6:$I$13,'S10'!$B$6:$B$13,$A34,'S10'!$E$6:$E$13,"Víctor")+SUMIFS('S10'!$I$6:$I$13,'S10'!$B$6:$B$13,$A34,'S10'!$E$6:$E$13,"Ambos")+SUMIFS('Holgura'!$I$6:$I$11,'Holgura'!$B$6:$B$11,$A34,'Holgura'!$E$6:$E$11,"Víctor")+SUMIFS('Holgura'!$I$6:$I$11,'Holgura'!$B$6:$B$11,$A34,'Holgura'!$E$6:$E$11,"Ambos")+SUMIFS('Entrega'!$I$6:$I$9,'Entrega'!$B$6:$B$9,$A34,'Entrega'!$E$6:$E$9,"Víctor")+SUMIFS('Entrega'!$I$6:$I$9,'Entrega'!$B$6:$B$9,$A34,'Entrega'!$E$6:$E$9,"Ambos")+SUMIFS('Defensa'!$I$6:$I$10,'Defensa'!$B$6:$B$10,$A34,'Defensa'!$E$6:$E$10,"Víctor")+SUMIFS('Defensa'!$I$6:$I$10,'Defensa'!$B$6:$B$10,$A34,'Defensa'!$E$6:$E$10,"Ambos")</f>
         <v/>
       </c>
       <c r="E34" s="21">
-        <f>SUMIFS('S1'!$I$6:$I$32,'S1'!$B$6:$B$32,$A34,'S1'!$E$6:$E$32,"Diego")+SUMIFS('S1'!$I$6:$I$32,'S1'!$B$6:$B$32,$A34,'S1'!$E$6:$E$32,"Ambos")+SUMIFS('S2'!$I$6:$I$23,'S2'!$B$6:$B$23,$A34,'S2'!$E$6:$E$23,"Diego")+SUMIFS('S2'!$I$6:$I$23,'S2'!$B$6:$B$23,$A34,'S2'!$E$6:$E$23,"Ambos")+SUMIFS('S3'!$I$6:$I$19,'S3'!$B$6:$B$19,$A34,'S3'!$E$6:$E$19,"Diego")+SUMIFS('S3'!$I$6:$I$19,'S3'!$B$6:$B$19,$A34,'S3'!$E$6:$E$19,"Ambos")+SUMIFS('S4'!$I$6:$I$20,'S4'!$B$6:$B$20,$A34,'S4'!$E$6:$E$20,"Diego")+SUMIFS('S4'!$I$6:$I$20,'S4'!$B$6:$B$20,$A34,'S4'!$E$6:$E$20,"Ambos")+SUMIFS('S5'!$I$6:$I$20,'S5'!$B$6:$B$20,$A34,'S5'!$E$6:$E$20,"Diego")+SUMIFS('S5'!$I$6:$I$20,'S5'!$B$6:$B$20,$A34,'S5'!$E$6:$E$20,"Ambos")+SUMIFS('S6'!$I$6:$I$17,'S6'!$B$6:$B$17,$A34,'S6'!$E$6:$E$17,"Diego")+SUMIFS('S6'!$I$6:$I$17,'S6'!$B$6:$B$17,$A34,'S6'!$E$6:$E$17,"Ambos")+SUMIFS('S7'!$I$6:$I$19,'S7'!$B$6:$B$19,$A34,'S7'!$E$6:$E$19,"Diego")+SUMIFS('S7'!$I$6:$I$19,'S7'!$B$6:$B$19,$A34,'S7'!$E$6:$E$19,"Ambos")+SUMIFS('S8'!$I$6:$I$23,'S8'!$B$6:$B$23,$A34,'S8'!$E$6:$E$23,"Diego")+SUMIFS('S8'!$I$6:$I$23,'S8'!$B$6:$B$23,$A34,'S8'!$E$6:$E$23,"Ambos")+SUMIFS('S9'!$I$6:$I$15,'S9'!$B$6:$B$15,$A34,'S9'!$E$6:$E$15,"Diego")+SUMIFS('S9'!$I$6:$I$15,'S9'!$B$6:$B$15,$A34,'S9'!$E$6:$E$15,"Ambos")+SUMIFS('S10'!$I$6:$I$13,'S10'!$B$6:$B$13,$A34,'S10'!$E$6:$E$13,"Diego")+SUMIFS('S10'!$I$6:$I$13,'S10'!$B$6:$B$13,$A34,'S10'!$E$6:$E$13,"Ambos")+SUMIFS('Holgura'!$I$6:$I$11,'Holgura'!$B$6:$B$11,$A34,'Holgura'!$E$6:$E$11,"Diego")+SUMIFS('Holgura'!$I$6:$I$11,'Holgura'!$B$6:$B$11,$A34,'Holgura'!$E$6:$E$11,"Ambos")+SUMIFS('Entrega'!$I$6:$I$9,'Entrega'!$B$6:$B$9,$A34,'Entrega'!$E$6:$E$9,"Diego")+SUMIFS('Entrega'!$I$6:$I$9,'Entrega'!$B$6:$B$9,$A34,'Entrega'!$E$6:$E$9,"Ambos")+SUMIFS('Defensa'!$I$6:$I$10,'Defensa'!$B$6:$B$10,$A34,'Defensa'!$E$6:$E$10,"Diego")+SUMIFS('Defensa'!$I$6:$I$10,'Defensa'!$B$6:$B$10,$A34,'Defensa'!$E$6:$E$10,"Ambos")</f>
+        <f>SUMIFS('S1'!$I$6:$I$32,'S1'!$B$6:$B$32,$A34,'S1'!$E$6:$E$32,"Diego")+SUMIFS('S1'!$I$6:$I$32,'S1'!$B$6:$B$32,$A34,'S1'!$E$6:$E$32,"Ambos")+SUMIFS('S2'!$I$6:$I$23,'S2'!$B$6:$B$23,$A34,'S2'!$E$6:$E$23,"Diego")+SUMIFS('S2'!$I$6:$I$23,'S2'!$B$6:$B$23,$A34,'S2'!$E$6:$E$23,"Ambos")+SUMIFS('S3'!$I$6:$I$24,'S3'!$B$6:$B$24,$A34,'S3'!$E$6:$E$24,"Diego")+SUMIFS('S3'!$I$6:$I$24,'S3'!$B$6:$B$24,$A34,'S3'!$E$6:$E$24,"Ambos")+SUMIFS('S4'!$I$6:$I$22,'S4'!$B$6:$B$22,$A34,'S4'!$E$6:$E$22,"Diego")+SUMIFS('S4'!$I$6:$I$22,'S4'!$B$6:$B$22,$A34,'S4'!$E$6:$E$22,"Ambos")+SUMIFS('S5'!$I$6:$I$20,'S5'!$B$6:$B$20,$A34,'S5'!$E$6:$E$20,"Diego")+SUMIFS('S5'!$I$6:$I$20,'S5'!$B$6:$B$20,$A34,'S5'!$E$6:$E$20,"Ambos")+SUMIFS('S6'!$I$6:$I$17,'S6'!$B$6:$B$17,$A34,'S6'!$E$6:$E$17,"Diego")+SUMIFS('S6'!$I$6:$I$17,'S6'!$B$6:$B$17,$A34,'S6'!$E$6:$E$17,"Ambos")+SUMIFS('S7'!$I$6:$I$19,'S7'!$B$6:$B$19,$A34,'S7'!$E$6:$E$19,"Diego")+SUMIFS('S7'!$I$6:$I$19,'S7'!$B$6:$B$19,$A34,'S7'!$E$6:$E$19,"Ambos")+SUMIFS('S8'!$I$6:$I$23,'S8'!$B$6:$B$23,$A34,'S8'!$E$6:$E$23,"Diego")+SUMIFS('S8'!$I$6:$I$23,'S8'!$B$6:$B$23,$A34,'S8'!$E$6:$E$23,"Ambos")+SUMIFS('S9'!$I$6:$I$15,'S9'!$B$6:$B$15,$A34,'S9'!$E$6:$E$15,"Diego")+SUMIFS('S9'!$I$6:$I$15,'S9'!$B$6:$B$15,$A34,'S9'!$E$6:$E$15,"Ambos")+SUMIFS('S10'!$I$6:$I$13,'S10'!$B$6:$B$13,$A34,'S10'!$E$6:$E$13,"Diego")+SUMIFS('S10'!$I$6:$I$13,'S10'!$B$6:$B$13,$A34,'S10'!$E$6:$E$13,"Ambos")+SUMIFS('Holgura'!$I$6:$I$11,'Holgura'!$B$6:$B$11,$A34,'Holgura'!$E$6:$E$11,"Diego")+SUMIFS('Holgura'!$I$6:$I$11,'Holgura'!$B$6:$B$11,$A34,'Holgura'!$E$6:$E$11,"Ambos")+SUMIFS('Entrega'!$I$6:$I$9,'Entrega'!$B$6:$B$9,$A34,'Entrega'!$E$6:$E$9,"Diego")+SUMIFS('Entrega'!$I$6:$I$9,'Entrega'!$B$6:$B$9,$A34,'Entrega'!$E$6:$E$9,"Ambos")+SUMIFS('Defensa'!$I$6:$I$10,'Defensa'!$B$6:$B$10,$A34,'Defensa'!$E$6:$E$10,"Diego")+SUMIFS('Defensa'!$I$6:$I$10,'Defensa'!$B$6:$B$10,$A34,'Defensa'!$E$6:$E$10,"Ambos")</f>
         <v/>
       </c>
       <c r="F34" s="21">
-        <f>COUNTIFS('S1'!$B$6:$B$32,$A34,'S1'!$E$6:$E$32,"Víctor")+COUNTIFS('S1'!$B$6:$B$32,$A34,'S1'!$E$6:$E$32,"Ambos")+COUNTIFS('S2'!$B$6:$B$23,$A34,'S2'!$E$6:$E$23,"Víctor")+COUNTIFS('S2'!$B$6:$B$23,$A34,'S2'!$E$6:$E$23,"Ambos")+COUNTIFS('S3'!$B$6:$B$19,$A34,'S3'!$E$6:$E$19,"Víctor")+COUNTIFS('S3'!$B$6:$B$19,$A34,'S3'!$E$6:$E$19,"Ambos")+COUNTIFS('S4'!$B$6:$B$20,$A34,'S4'!$E$6:$E$20,"Víctor")+COUNTIFS('S4'!$B$6:$B$20,$A34,'S4'!$E$6:$E$20,"Ambos")+COUNTIFS('S5'!$B$6:$B$20,$A34,'S5'!$E$6:$E$20,"Víctor")+COUNTIFS('S5'!$B$6:$B$20,$A34,'S5'!$E$6:$E$20,"Ambos")+COUNTIFS('S6'!$B$6:$B$17,$A34,'S6'!$E$6:$E$17,"Víctor")+COUNTIFS('S6'!$B$6:$B$17,$A34,'S6'!$E$6:$E$17,"Ambos")+COUNTIFS('S7'!$B$6:$B$19,$A34,'S7'!$E$6:$E$19,"Víctor")+COUNTIFS('S7'!$B$6:$B$19,$A34,'S7'!$E$6:$E$19,"Ambos")+COUNTIFS('S8'!$B$6:$B$23,$A34,'S8'!$E$6:$E$23,"Víctor")+COUNTIFS('S8'!$B$6:$B$23,$A34,'S8'!$E$6:$E$23,"Ambos")+COUNTIFS('S9'!$B$6:$B$15,$A34,'S9'!$E$6:$E$15,"Víctor")+COUNTIFS('S9'!$B$6:$B$15,$A34,'S9'!$E$6:$E$15,"Ambos")+COUNTIFS('S10'!$B$6:$B$13,$A34,'S10'!$E$6:$E$13,"Víctor")+COUNTIFS('S10'!$B$6:$B$13,$A34,'S10'!$E$6:$E$13,"Ambos")+COUNTIFS('Holgura'!$B$6:$B$11,$A34,'Holgura'!$E$6:$E$11,"Víctor")+COUNTIFS('Holgura'!$B$6:$B$11,$A34,'Holgura'!$E$6:$E$11,"Ambos")+COUNTIFS('Entrega'!$B$6:$B$9,$A34,'Entrega'!$E$6:$E$9,"Víctor")+COUNTIFS('Entrega'!$B$6:$B$9,$A34,'Entrega'!$E$6:$E$9,"Ambos")+COUNTIFS('Defensa'!$B$6:$B$10,$A34,'Defensa'!$E$6:$E$10,"Víctor")+COUNTIFS('Defensa'!$B$6:$B$10,$A34,'Defensa'!$E$6:$E$10,"Ambos")</f>
+        <f>COUNTIFS('S1'!$B$6:$B$32,$A34,'S1'!$E$6:$E$32,"Víctor")+COUNTIFS('S1'!$B$6:$B$32,$A34,'S1'!$E$6:$E$32,"Ambos")+COUNTIFS('S2'!$B$6:$B$23,$A34,'S2'!$E$6:$E$23,"Víctor")+COUNTIFS('S2'!$B$6:$B$23,$A34,'S2'!$E$6:$E$23,"Ambos")+COUNTIFS('S3'!$B$6:$B$24,$A34,'S3'!$E$6:$E$24,"Víctor")+COUNTIFS('S3'!$B$6:$B$24,$A34,'S3'!$E$6:$E$24,"Ambos")+COUNTIFS('S4'!$B$6:$B$22,$A34,'S4'!$E$6:$E$22,"Víctor")+COUNTIFS('S4'!$B$6:$B$22,$A34,'S4'!$E$6:$E$22,"Ambos")+COUNTIFS('S5'!$B$6:$B$20,$A34,'S5'!$E$6:$E$20,"Víctor")+COUNTIFS('S5'!$B$6:$B$20,$A34,'S5'!$E$6:$E$20,"Ambos")+COUNTIFS('S6'!$B$6:$B$17,$A34,'S6'!$E$6:$E$17,"Víctor")+COUNTIFS('S6'!$B$6:$B$17,$A34,'S6'!$E$6:$E$17,"Ambos")+COUNTIFS('S7'!$B$6:$B$19,$A34,'S7'!$E$6:$E$19,"Víctor")+COUNTIFS('S7'!$B$6:$B$19,$A34,'S7'!$E$6:$E$19,"Ambos")+COUNTIFS('S8'!$B$6:$B$23,$A34,'S8'!$E$6:$E$23,"Víctor")+COUNTIFS('S8'!$B$6:$B$23,$A34,'S8'!$E$6:$E$23,"Ambos")+COUNTIFS('S9'!$B$6:$B$15,$A34,'S9'!$E$6:$E$15,"Víctor")+COUNTIFS('S9'!$B$6:$B$15,$A34,'S9'!$E$6:$E$15,"Ambos")+COUNTIFS('S10'!$B$6:$B$13,$A34,'S10'!$E$6:$E$13,"Víctor")+COUNTIFS('S10'!$B$6:$B$13,$A34,'S10'!$E$6:$E$13,"Ambos")+COUNTIFS('Holgura'!$B$6:$B$11,$A34,'Holgura'!$E$6:$E$11,"Víctor")+COUNTIFS('Holgura'!$B$6:$B$11,$A34,'Holgura'!$E$6:$E$11,"Ambos")+COUNTIFS('Entrega'!$B$6:$B$9,$A34,'Entrega'!$E$6:$E$9,"Víctor")+COUNTIFS('Entrega'!$B$6:$B$9,$A34,'Entrega'!$E$6:$E$9,"Ambos")+COUNTIFS('Defensa'!$B$6:$B$10,$A34,'Defensa'!$E$6:$E$10,"Víctor")+COUNTIFS('Defensa'!$B$6:$B$10,$A34,'Defensa'!$E$6:$E$10,"Ambos")</f>
         <v/>
       </c>
       <c r="G34" s="21">
-        <f>COUNTIFS('S1'!$B$6:$B$32,$A34,'S1'!$E$6:$E$32,"Diego")+COUNTIFS('S1'!$B$6:$B$32,$A34,'S1'!$E$6:$E$32,"Ambos")+COUNTIFS('S2'!$B$6:$B$23,$A34,'S2'!$E$6:$E$23,"Diego")+COUNTIFS('S2'!$B$6:$B$23,$A34,'S2'!$E$6:$E$23,"Ambos")+COUNTIFS('S3'!$B$6:$B$19,$A34,'S3'!$E$6:$E$19,"Diego")+COUNTIFS('S3'!$B$6:$B$19,$A34,'S3'!$E$6:$E$19,"Ambos")+COUNTIFS('S4'!$B$6:$B$20,$A34,'S4'!$E$6:$E$20,"Diego")+COUNTIFS('S4'!$B$6:$B$20,$A34,'S4'!$E$6:$E$20,"Ambos")+COUNTIFS('S5'!$B$6:$B$20,$A34,'S5'!$E$6:$E$20,"Diego")+COUNTIFS('S5'!$B$6:$B$20,$A34,'S5'!$E$6:$E$20,"Ambos")+COUNTIFS('S6'!$B$6:$B$17,$A34,'S6'!$E$6:$E$17,"Diego")+COUNTIFS('S6'!$B$6:$B$17,$A34,'S6'!$E$6:$E$17,"Ambos")+COUNTIFS('S7'!$B$6:$B$19,$A34,'S7'!$E$6:$E$19,"Diego")+COUNTIFS('S7'!$B$6:$B$19,$A34,'S7'!$E$6:$E$19,"Ambos")+COUNTIFS('S8'!$B$6:$B$23,$A34,'S8'!$E$6:$E$23,"Diego")+COUNTIFS('S8'!$B$6:$B$23,$A34,'S8'!$E$6:$E$23,"Ambos")+COUNTIFS('S9'!$B$6:$B$15,$A34,'S9'!$E$6:$E$15,"Diego")+COUNTIFS('S9'!$B$6:$B$15,$A34,'S9'!$E$6:$E$15,"Ambos")+COUNTIFS('S10'!$B$6:$B$13,$A34,'S10'!$E$6:$E$13,"Diego")+COUNTIFS('S10'!$B$6:$B$13,$A34,'S10'!$E$6:$E$13,"Ambos")+COUNTIFS('Holgura'!$B$6:$B$11,$A34,'Holgura'!$E$6:$E$11,"Diego")+COUNTIFS('Holgura'!$B$6:$B$11,$A34,'Holgura'!$E$6:$E$11,"Ambos")+COUNTIFS('Entrega'!$B$6:$B$9,$A34,'Entrega'!$E$6:$E$9,"Diego")+COUNTIFS('Entrega'!$B$6:$B$9,$A34,'Entrega'!$E$6:$E$9,"Ambos")+COUNTIFS('Defensa'!$B$6:$B$10,$A34,'Defensa'!$E$6:$E$10,"Diego")+COUNTIFS('Defensa'!$B$6:$B$10,$A34,'Defensa'!$E$6:$E$10,"Ambos")</f>
+        <f>COUNTIFS('S1'!$B$6:$B$32,$A34,'S1'!$E$6:$E$32,"Diego")+COUNTIFS('S1'!$B$6:$B$32,$A34,'S1'!$E$6:$E$32,"Ambos")+COUNTIFS('S2'!$B$6:$B$23,$A34,'S2'!$E$6:$E$23,"Diego")+COUNTIFS('S2'!$B$6:$B$23,$A34,'S2'!$E$6:$E$23,"Ambos")+COUNTIFS('S3'!$B$6:$B$24,$A34,'S3'!$E$6:$E$24,"Diego")+COUNTIFS('S3'!$B$6:$B$24,$A34,'S3'!$E$6:$E$24,"Ambos")+COUNTIFS('S4'!$B$6:$B$22,$A34,'S4'!$E$6:$E$22,"Diego")+COUNTIFS('S4'!$B$6:$B$22,$A34,'S4'!$E$6:$E$22,"Ambos")+COUNTIFS('S5'!$B$6:$B$20,$A34,'S5'!$E$6:$E$20,"Diego")+COUNTIFS('S5'!$B$6:$B$20,$A34,'S5'!$E$6:$E$20,"Ambos")+COUNTIFS('S6'!$B$6:$B$17,$A34,'S6'!$E$6:$E$17,"Diego")+COUNTIFS('S6'!$B$6:$B$17,$A34,'S6'!$E$6:$E$17,"Ambos")+COUNTIFS('S7'!$B$6:$B$19,$A34,'S7'!$E$6:$E$19,"Diego")+COUNTIFS('S7'!$B$6:$B$19,$A34,'S7'!$E$6:$E$19,"Ambos")+COUNTIFS('S8'!$B$6:$B$23,$A34,'S8'!$E$6:$E$23,"Diego")+COUNTIFS('S8'!$B$6:$B$23,$A34,'S8'!$E$6:$E$23,"Ambos")+COUNTIFS('S9'!$B$6:$B$15,$A34,'S9'!$E$6:$E$15,"Diego")+COUNTIFS('S9'!$B$6:$B$15,$A34,'S9'!$E$6:$E$15,"Ambos")+COUNTIFS('S10'!$B$6:$B$13,$A34,'S10'!$E$6:$E$13,"Diego")+COUNTIFS('S10'!$B$6:$B$13,$A34,'S10'!$E$6:$E$13,"Ambos")+COUNTIFS('Holgura'!$B$6:$B$11,$A34,'Holgura'!$E$6:$E$11,"Diego")+COUNTIFS('Holgura'!$B$6:$B$11,$A34,'Holgura'!$E$6:$E$11,"Ambos")+COUNTIFS('Entrega'!$B$6:$B$9,$A34,'Entrega'!$E$6:$E$9,"Diego")+COUNTIFS('Entrega'!$B$6:$B$9,$A34,'Entrega'!$E$6:$E$9,"Ambos")+COUNTIFS('Defensa'!$B$6:$B$10,$A34,'Defensa'!$E$6:$E$10,"Diego")+COUNTIFS('Defensa'!$B$6:$B$10,$A34,'Defensa'!$E$6:$E$10,"Ambos")</f>
         <v/>
       </c>
     </row>
@@ -9550,19 +9571,19 @@
         <v/>
       </c>
       <c r="D35" s="21">
-        <f>SUMIFS('S1'!$I$6:$I$32,'S1'!$B$6:$B$32,$A35,'S1'!$E$6:$E$32,"Víctor")+SUMIFS('S1'!$I$6:$I$32,'S1'!$B$6:$B$32,$A35,'S1'!$E$6:$E$32,"Ambos")+SUMIFS('S2'!$I$6:$I$23,'S2'!$B$6:$B$23,$A35,'S2'!$E$6:$E$23,"Víctor")+SUMIFS('S2'!$I$6:$I$23,'S2'!$B$6:$B$23,$A35,'S2'!$E$6:$E$23,"Ambos")+SUMIFS('S3'!$I$6:$I$19,'S3'!$B$6:$B$19,$A35,'S3'!$E$6:$E$19,"Víctor")+SUMIFS('S3'!$I$6:$I$19,'S3'!$B$6:$B$19,$A35,'S3'!$E$6:$E$19,"Ambos")+SUMIFS('S4'!$I$6:$I$20,'S4'!$B$6:$B$20,$A35,'S4'!$E$6:$E$20,"Víctor")+SUMIFS('S4'!$I$6:$I$20,'S4'!$B$6:$B$20,$A35,'S4'!$E$6:$E$20,"Ambos")+SUMIFS('S5'!$I$6:$I$20,'S5'!$B$6:$B$20,$A35,'S5'!$E$6:$E$20,"Víctor")+SUMIFS('S5'!$I$6:$I$20,'S5'!$B$6:$B$20,$A35,'S5'!$E$6:$E$20,"Ambos")+SUMIFS('S6'!$I$6:$I$17,'S6'!$B$6:$B$17,$A35,'S6'!$E$6:$E$17,"Víctor")+SUMIFS('S6'!$I$6:$I$17,'S6'!$B$6:$B$17,$A35,'S6'!$E$6:$E$17,"Ambos")+SUMIFS('S7'!$I$6:$I$19,'S7'!$B$6:$B$19,$A35,'S7'!$E$6:$E$19,"Víctor")+SUMIFS('S7'!$I$6:$I$19,'S7'!$B$6:$B$19,$A35,'S7'!$E$6:$E$19,"Ambos")+SUMIFS('S8'!$I$6:$I$23,'S8'!$B$6:$B$23,$A35,'S8'!$E$6:$E$23,"Víctor")+SUMIFS('S8'!$I$6:$I$23,'S8'!$B$6:$B$23,$A35,'S8'!$E$6:$E$23,"Ambos")+SUMIFS('S9'!$I$6:$I$15,'S9'!$B$6:$B$15,$A35,'S9'!$E$6:$E$15,"Víctor")+SUMIFS('S9'!$I$6:$I$15,'S9'!$B$6:$B$15,$A35,'S9'!$E$6:$E$15,"Ambos")+SUMIFS('S10'!$I$6:$I$13,'S10'!$B$6:$B$13,$A35,'S10'!$E$6:$E$13,"Víctor")+SUMIFS('S10'!$I$6:$I$13,'S10'!$B$6:$B$13,$A35,'S10'!$E$6:$E$13,"Ambos")+SUMIFS('Holgura'!$I$6:$I$11,'Holgura'!$B$6:$B$11,$A35,'Holgura'!$E$6:$E$11,"Víctor")+SUMIFS('Holgura'!$I$6:$I$11,'Holgura'!$B$6:$B$11,$A35,'Holgura'!$E$6:$E$11,"Ambos")+SUMIFS('Entrega'!$I$6:$I$9,'Entrega'!$B$6:$B$9,$A35,'Entrega'!$E$6:$E$9,"Víctor")+SUMIFS('Entrega'!$I$6:$I$9,'Entrega'!$B$6:$B$9,$A35,'Entrega'!$E$6:$E$9,"Ambos")+SUMIFS('Defensa'!$I$6:$I$10,'Defensa'!$B$6:$B$10,$A35,'Defensa'!$E$6:$E$10,"Víctor")+SUMIFS('Defensa'!$I$6:$I$10,'Defensa'!$B$6:$B$10,$A35,'Defensa'!$E$6:$E$10,"Ambos")</f>
+        <f>SUMIFS('S1'!$I$6:$I$32,'S1'!$B$6:$B$32,$A35,'S1'!$E$6:$E$32,"Víctor")+SUMIFS('S1'!$I$6:$I$32,'S1'!$B$6:$B$32,$A35,'S1'!$E$6:$E$32,"Ambos")+SUMIFS('S2'!$I$6:$I$23,'S2'!$B$6:$B$23,$A35,'S2'!$E$6:$E$23,"Víctor")+SUMIFS('S2'!$I$6:$I$23,'S2'!$B$6:$B$23,$A35,'S2'!$E$6:$E$23,"Ambos")+SUMIFS('S3'!$I$6:$I$24,'S3'!$B$6:$B$24,$A35,'S3'!$E$6:$E$24,"Víctor")+SUMIFS('S3'!$I$6:$I$24,'S3'!$B$6:$B$24,$A35,'S3'!$E$6:$E$24,"Ambos")+SUMIFS('S4'!$I$6:$I$22,'S4'!$B$6:$B$22,$A35,'S4'!$E$6:$E$22,"Víctor")+SUMIFS('S4'!$I$6:$I$22,'S4'!$B$6:$B$22,$A35,'S4'!$E$6:$E$22,"Ambos")+SUMIFS('S5'!$I$6:$I$20,'S5'!$B$6:$B$20,$A35,'S5'!$E$6:$E$20,"Víctor")+SUMIFS('S5'!$I$6:$I$20,'S5'!$B$6:$B$20,$A35,'S5'!$E$6:$E$20,"Ambos")+SUMIFS('S6'!$I$6:$I$17,'S6'!$B$6:$B$17,$A35,'S6'!$E$6:$E$17,"Víctor")+SUMIFS('S6'!$I$6:$I$17,'S6'!$B$6:$B$17,$A35,'S6'!$E$6:$E$17,"Ambos")+SUMIFS('S7'!$I$6:$I$19,'S7'!$B$6:$B$19,$A35,'S7'!$E$6:$E$19,"Víctor")+SUMIFS('S7'!$I$6:$I$19,'S7'!$B$6:$B$19,$A35,'S7'!$E$6:$E$19,"Ambos")+SUMIFS('S8'!$I$6:$I$23,'S8'!$B$6:$B$23,$A35,'S8'!$E$6:$E$23,"Víctor")+SUMIFS('S8'!$I$6:$I$23,'S8'!$B$6:$B$23,$A35,'S8'!$E$6:$E$23,"Ambos")+SUMIFS('S9'!$I$6:$I$15,'S9'!$B$6:$B$15,$A35,'S9'!$E$6:$E$15,"Víctor")+SUMIFS('S9'!$I$6:$I$15,'S9'!$B$6:$B$15,$A35,'S9'!$E$6:$E$15,"Ambos")+SUMIFS('S10'!$I$6:$I$13,'S10'!$B$6:$B$13,$A35,'S10'!$E$6:$E$13,"Víctor")+SUMIFS('S10'!$I$6:$I$13,'S10'!$B$6:$B$13,$A35,'S10'!$E$6:$E$13,"Ambos")+SUMIFS('Holgura'!$I$6:$I$11,'Holgura'!$B$6:$B$11,$A35,'Holgura'!$E$6:$E$11,"Víctor")+SUMIFS('Holgura'!$I$6:$I$11,'Holgura'!$B$6:$B$11,$A35,'Holgura'!$E$6:$E$11,"Ambos")+SUMIFS('Entrega'!$I$6:$I$9,'Entrega'!$B$6:$B$9,$A35,'Entrega'!$E$6:$E$9,"Víctor")+SUMIFS('Entrega'!$I$6:$I$9,'Entrega'!$B$6:$B$9,$A35,'Entrega'!$E$6:$E$9,"Ambos")+SUMIFS('Defensa'!$I$6:$I$10,'Defensa'!$B$6:$B$10,$A35,'Defensa'!$E$6:$E$10,"Víctor")+SUMIFS('Defensa'!$I$6:$I$10,'Defensa'!$B$6:$B$10,$A35,'Defensa'!$E$6:$E$10,"Ambos")</f>
         <v/>
       </c>
       <c r="E35" s="21">
-        <f>SUMIFS('S1'!$I$6:$I$32,'S1'!$B$6:$B$32,$A35,'S1'!$E$6:$E$32,"Diego")+SUMIFS('S1'!$I$6:$I$32,'S1'!$B$6:$B$32,$A35,'S1'!$E$6:$E$32,"Ambos")+SUMIFS('S2'!$I$6:$I$23,'S2'!$B$6:$B$23,$A35,'S2'!$E$6:$E$23,"Diego")+SUMIFS('S2'!$I$6:$I$23,'S2'!$B$6:$B$23,$A35,'S2'!$E$6:$E$23,"Ambos")+SUMIFS('S3'!$I$6:$I$19,'S3'!$B$6:$B$19,$A35,'S3'!$E$6:$E$19,"Diego")+SUMIFS('S3'!$I$6:$I$19,'S3'!$B$6:$B$19,$A35,'S3'!$E$6:$E$19,"Ambos")+SUMIFS('S4'!$I$6:$I$20,'S4'!$B$6:$B$20,$A35,'S4'!$E$6:$E$20,"Diego")+SUMIFS('S4'!$I$6:$I$20,'S4'!$B$6:$B$20,$A35,'S4'!$E$6:$E$20,"Ambos")+SUMIFS('S5'!$I$6:$I$20,'S5'!$B$6:$B$20,$A35,'S5'!$E$6:$E$20,"Diego")+SUMIFS('S5'!$I$6:$I$20,'S5'!$B$6:$B$20,$A35,'S5'!$E$6:$E$20,"Ambos")+SUMIFS('S6'!$I$6:$I$17,'S6'!$B$6:$B$17,$A35,'S6'!$E$6:$E$17,"Diego")+SUMIFS('S6'!$I$6:$I$17,'S6'!$B$6:$B$17,$A35,'S6'!$E$6:$E$17,"Ambos")+SUMIFS('S7'!$I$6:$I$19,'S7'!$B$6:$B$19,$A35,'S7'!$E$6:$E$19,"Diego")+SUMIFS('S7'!$I$6:$I$19,'S7'!$B$6:$B$19,$A35,'S7'!$E$6:$E$19,"Ambos")+SUMIFS('S8'!$I$6:$I$23,'S8'!$B$6:$B$23,$A35,'S8'!$E$6:$E$23,"Diego")+SUMIFS('S8'!$I$6:$I$23,'S8'!$B$6:$B$23,$A35,'S8'!$E$6:$E$23,"Ambos")+SUMIFS('S9'!$I$6:$I$15,'S9'!$B$6:$B$15,$A35,'S9'!$E$6:$E$15,"Diego")+SUMIFS('S9'!$I$6:$I$15,'S9'!$B$6:$B$15,$A35,'S9'!$E$6:$E$15,"Ambos")+SUMIFS('S10'!$I$6:$I$13,'S10'!$B$6:$B$13,$A35,'S10'!$E$6:$E$13,"Diego")+SUMIFS('S10'!$I$6:$I$13,'S10'!$B$6:$B$13,$A35,'S10'!$E$6:$E$13,"Ambos")+SUMIFS('Holgura'!$I$6:$I$11,'Holgura'!$B$6:$B$11,$A35,'Holgura'!$E$6:$E$11,"Diego")+SUMIFS('Holgura'!$I$6:$I$11,'Holgura'!$B$6:$B$11,$A35,'Holgura'!$E$6:$E$11,"Ambos")+SUMIFS('Entrega'!$I$6:$I$9,'Entrega'!$B$6:$B$9,$A35,'Entrega'!$E$6:$E$9,"Diego")+SUMIFS('Entrega'!$I$6:$I$9,'Entrega'!$B$6:$B$9,$A35,'Entrega'!$E$6:$E$9,"Ambos")+SUMIFS('Defensa'!$I$6:$I$10,'Defensa'!$B$6:$B$10,$A35,'Defensa'!$E$6:$E$10,"Diego")+SUMIFS('Defensa'!$I$6:$I$10,'Defensa'!$B$6:$B$10,$A35,'Defensa'!$E$6:$E$10,"Ambos")</f>
+        <f>SUMIFS('S1'!$I$6:$I$32,'S1'!$B$6:$B$32,$A35,'S1'!$E$6:$E$32,"Diego")+SUMIFS('S1'!$I$6:$I$32,'S1'!$B$6:$B$32,$A35,'S1'!$E$6:$E$32,"Ambos")+SUMIFS('S2'!$I$6:$I$23,'S2'!$B$6:$B$23,$A35,'S2'!$E$6:$E$23,"Diego")+SUMIFS('S2'!$I$6:$I$23,'S2'!$B$6:$B$23,$A35,'S2'!$E$6:$E$23,"Ambos")+SUMIFS('S3'!$I$6:$I$24,'S3'!$B$6:$B$24,$A35,'S3'!$E$6:$E$24,"Diego")+SUMIFS('S3'!$I$6:$I$24,'S3'!$B$6:$B$24,$A35,'S3'!$E$6:$E$24,"Ambos")+SUMIFS('S4'!$I$6:$I$22,'S4'!$B$6:$B$22,$A35,'S4'!$E$6:$E$22,"Diego")+SUMIFS('S4'!$I$6:$I$22,'S4'!$B$6:$B$22,$A35,'S4'!$E$6:$E$22,"Ambos")+SUMIFS('S5'!$I$6:$I$20,'S5'!$B$6:$B$20,$A35,'S5'!$E$6:$E$20,"Diego")+SUMIFS('S5'!$I$6:$I$20,'S5'!$B$6:$B$20,$A35,'S5'!$E$6:$E$20,"Ambos")+SUMIFS('S6'!$I$6:$I$17,'S6'!$B$6:$B$17,$A35,'S6'!$E$6:$E$17,"Diego")+SUMIFS('S6'!$I$6:$I$17,'S6'!$B$6:$B$17,$A35,'S6'!$E$6:$E$17,"Ambos")+SUMIFS('S7'!$I$6:$I$19,'S7'!$B$6:$B$19,$A35,'S7'!$E$6:$E$19,"Diego")+SUMIFS('S7'!$I$6:$I$19,'S7'!$B$6:$B$19,$A35,'S7'!$E$6:$E$19,"Ambos")+SUMIFS('S8'!$I$6:$I$23,'S8'!$B$6:$B$23,$A35,'S8'!$E$6:$E$23,"Diego")+SUMIFS('S8'!$I$6:$I$23,'S8'!$B$6:$B$23,$A35,'S8'!$E$6:$E$23,"Ambos")+SUMIFS('S9'!$I$6:$I$15,'S9'!$B$6:$B$15,$A35,'S9'!$E$6:$E$15,"Diego")+SUMIFS('S9'!$I$6:$I$15,'S9'!$B$6:$B$15,$A35,'S9'!$E$6:$E$15,"Ambos")+SUMIFS('S10'!$I$6:$I$13,'S10'!$B$6:$B$13,$A35,'S10'!$E$6:$E$13,"Diego")+SUMIFS('S10'!$I$6:$I$13,'S10'!$B$6:$B$13,$A35,'S10'!$E$6:$E$13,"Ambos")+SUMIFS('Holgura'!$I$6:$I$11,'Holgura'!$B$6:$B$11,$A35,'Holgura'!$E$6:$E$11,"Diego")+SUMIFS('Holgura'!$I$6:$I$11,'Holgura'!$B$6:$B$11,$A35,'Holgura'!$E$6:$E$11,"Ambos")+SUMIFS('Entrega'!$I$6:$I$9,'Entrega'!$B$6:$B$9,$A35,'Entrega'!$E$6:$E$9,"Diego")+SUMIFS('Entrega'!$I$6:$I$9,'Entrega'!$B$6:$B$9,$A35,'Entrega'!$E$6:$E$9,"Ambos")+SUMIFS('Defensa'!$I$6:$I$10,'Defensa'!$B$6:$B$10,$A35,'Defensa'!$E$6:$E$10,"Diego")+SUMIFS('Defensa'!$I$6:$I$10,'Defensa'!$B$6:$B$10,$A35,'Defensa'!$E$6:$E$10,"Ambos")</f>
         <v/>
       </c>
       <c r="F35" s="21">
-        <f>COUNTIFS('S1'!$B$6:$B$32,$A35,'S1'!$E$6:$E$32,"Víctor")+COUNTIFS('S1'!$B$6:$B$32,$A35,'S1'!$E$6:$E$32,"Ambos")+COUNTIFS('S2'!$B$6:$B$23,$A35,'S2'!$E$6:$E$23,"Víctor")+COUNTIFS('S2'!$B$6:$B$23,$A35,'S2'!$E$6:$E$23,"Ambos")+COUNTIFS('S3'!$B$6:$B$19,$A35,'S3'!$E$6:$E$19,"Víctor")+COUNTIFS('S3'!$B$6:$B$19,$A35,'S3'!$E$6:$E$19,"Ambos")+COUNTIFS('S4'!$B$6:$B$20,$A35,'S4'!$E$6:$E$20,"Víctor")+COUNTIFS('S4'!$B$6:$B$20,$A35,'S4'!$E$6:$E$20,"Ambos")+COUNTIFS('S5'!$B$6:$B$20,$A35,'S5'!$E$6:$E$20,"Víctor")+COUNTIFS('S5'!$B$6:$B$20,$A35,'S5'!$E$6:$E$20,"Ambos")+COUNTIFS('S6'!$B$6:$B$17,$A35,'S6'!$E$6:$E$17,"Víctor")+COUNTIFS('S6'!$B$6:$B$17,$A35,'S6'!$E$6:$E$17,"Ambos")+COUNTIFS('S7'!$B$6:$B$19,$A35,'S7'!$E$6:$E$19,"Víctor")+COUNTIFS('S7'!$B$6:$B$19,$A35,'S7'!$E$6:$E$19,"Ambos")+COUNTIFS('S8'!$B$6:$B$23,$A35,'S8'!$E$6:$E$23,"Víctor")+COUNTIFS('S8'!$B$6:$B$23,$A35,'S8'!$E$6:$E$23,"Ambos")+COUNTIFS('S9'!$B$6:$B$15,$A35,'S9'!$E$6:$E$15,"Víctor")+COUNTIFS('S9'!$B$6:$B$15,$A35,'S9'!$E$6:$E$15,"Ambos")+COUNTIFS('S10'!$B$6:$B$13,$A35,'S10'!$E$6:$E$13,"Víctor")+COUNTIFS('S10'!$B$6:$B$13,$A35,'S10'!$E$6:$E$13,"Ambos")+COUNTIFS('Holgura'!$B$6:$B$11,$A35,'Holgura'!$E$6:$E$11,"Víctor")+COUNTIFS('Holgura'!$B$6:$B$11,$A35,'Holgura'!$E$6:$E$11,"Ambos")+COUNTIFS('Entrega'!$B$6:$B$9,$A35,'Entrega'!$E$6:$E$9,"Víctor")+COUNTIFS('Entrega'!$B$6:$B$9,$A35,'Entrega'!$E$6:$E$9,"Ambos")+COUNTIFS('Defensa'!$B$6:$B$10,$A35,'Defensa'!$E$6:$E$10,"Víctor")+COUNTIFS('Defensa'!$B$6:$B$10,$A35,'Defensa'!$E$6:$E$10,"Ambos")</f>
+        <f>COUNTIFS('S1'!$B$6:$B$32,$A35,'S1'!$E$6:$E$32,"Víctor")+COUNTIFS('S1'!$B$6:$B$32,$A35,'S1'!$E$6:$E$32,"Ambos")+COUNTIFS('S2'!$B$6:$B$23,$A35,'S2'!$E$6:$E$23,"Víctor")+COUNTIFS('S2'!$B$6:$B$23,$A35,'S2'!$E$6:$E$23,"Ambos")+COUNTIFS('S3'!$B$6:$B$24,$A35,'S3'!$E$6:$E$24,"Víctor")+COUNTIFS('S3'!$B$6:$B$24,$A35,'S3'!$E$6:$E$24,"Ambos")+COUNTIFS('S4'!$B$6:$B$22,$A35,'S4'!$E$6:$E$22,"Víctor")+COUNTIFS('S4'!$B$6:$B$22,$A35,'S4'!$E$6:$E$22,"Ambos")+COUNTIFS('S5'!$B$6:$B$20,$A35,'S5'!$E$6:$E$20,"Víctor")+COUNTIFS('S5'!$B$6:$B$20,$A35,'S5'!$E$6:$E$20,"Ambos")+COUNTIFS('S6'!$B$6:$B$17,$A35,'S6'!$E$6:$E$17,"Víctor")+COUNTIFS('S6'!$B$6:$B$17,$A35,'S6'!$E$6:$E$17,"Ambos")+COUNTIFS('S7'!$B$6:$B$19,$A35,'S7'!$E$6:$E$19,"Víctor")+COUNTIFS('S7'!$B$6:$B$19,$A35,'S7'!$E$6:$E$19,"Ambos")+COUNTIFS('S8'!$B$6:$B$23,$A35,'S8'!$E$6:$E$23,"Víctor")+COUNTIFS('S8'!$B$6:$B$23,$A35,'S8'!$E$6:$E$23,"Ambos")+COUNTIFS('S9'!$B$6:$B$15,$A35,'S9'!$E$6:$E$15,"Víctor")+COUNTIFS('S9'!$B$6:$B$15,$A35,'S9'!$E$6:$E$15,"Ambos")+COUNTIFS('S10'!$B$6:$B$13,$A35,'S10'!$E$6:$E$13,"Víctor")+COUNTIFS('S10'!$B$6:$B$13,$A35,'S10'!$E$6:$E$13,"Ambos")+COUNTIFS('Holgura'!$B$6:$B$11,$A35,'Holgura'!$E$6:$E$11,"Víctor")+COUNTIFS('Holgura'!$B$6:$B$11,$A35,'Holgura'!$E$6:$E$11,"Ambos")+COUNTIFS('Entrega'!$B$6:$B$9,$A35,'Entrega'!$E$6:$E$9,"Víctor")+COUNTIFS('Entrega'!$B$6:$B$9,$A35,'Entrega'!$E$6:$E$9,"Ambos")+COUNTIFS('Defensa'!$B$6:$B$10,$A35,'Defensa'!$E$6:$E$10,"Víctor")+COUNTIFS('Defensa'!$B$6:$B$10,$A35,'Defensa'!$E$6:$E$10,"Ambos")</f>
         <v/>
       </c>
       <c r="G35" s="21">
-        <f>COUNTIFS('S1'!$B$6:$B$32,$A35,'S1'!$E$6:$E$32,"Diego")+COUNTIFS('S1'!$B$6:$B$32,$A35,'S1'!$E$6:$E$32,"Ambos")+COUNTIFS('S2'!$B$6:$B$23,$A35,'S2'!$E$6:$E$23,"Diego")+COUNTIFS('S2'!$B$6:$B$23,$A35,'S2'!$E$6:$E$23,"Ambos")+COUNTIFS('S3'!$B$6:$B$19,$A35,'S3'!$E$6:$E$19,"Diego")+COUNTIFS('S3'!$B$6:$B$19,$A35,'S3'!$E$6:$E$19,"Ambos")+COUNTIFS('S4'!$B$6:$B$20,$A35,'S4'!$E$6:$E$20,"Diego")+COUNTIFS('S4'!$B$6:$B$20,$A35,'S4'!$E$6:$E$20,"Ambos")+COUNTIFS('S5'!$B$6:$B$20,$A35,'S5'!$E$6:$E$20,"Diego")+COUNTIFS('S5'!$B$6:$B$20,$A35,'S5'!$E$6:$E$20,"Ambos")+COUNTIFS('S6'!$B$6:$B$17,$A35,'S6'!$E$6:$E$17,"Diego")+COUNTIFS('S6'!$B$6:$B$17,$A35,'S6'!$E$6:$E$17,"Ambos")+COUNTIFS('S7'!$B$6:$B$19,$A35,'S7'!$E$6:$E$19,"Diego")+COUNTIFS('S7'!$B$6:$B$19,$A35,'S7'!$E$6:$E$19,"Ambos")+COUNTIFS('S8'!$B$6:$B$23,$A35,'S8'!$E$6:$E$23,"Diego")+COUNTIFS('S8'!$B$6:$B$23,$A35,'S8'!$E$6:$E$23,"Ambos")+COUNTIFS('S9'!$B$6:$B$15,$A35,'S9'!$E$6:$E$15,"Diego")+COUNTIFS('S9'!$B$6:$B$15,$A35,'S9'!$E$6:$E$15,"Ambos")+COUNTIFS('S10'!$B$6:$B$13,$A35,'S10'!$E$6:$E$13,"Diego")+COUNTIFS('S10'!$B$6:$B$13,$A35,'S10'!$E$6:$E$13,"Ambos")+COUNTIFS('Holgura'!$B$6:$B$11,$A35,'Holgura'!$E$6:$E$11,"Diego")+COUNTIFS('Holgura'!$B$6:$B$11,$A35,'Holgura'!$E$6:$E$11,"Ambos")+COUNTIFS('Entrega'!$B$6:$B$9,$A35,'Entrega'!$E$6:$E$9,"Diego")+COUNTIFS('Entrega'!$B$6:$B$9,$A35,'Entrega'!$E$6:$E$9,"Ambos")+COUNTIFS('Defensa'!$B$6:$B$10,$A35,'Defensa'!$E$6:$E$10,"Diego")+COUNTIFS('Defensa'!$B$6:$B$10,$A35,'Defensa'!$E$6:$E$10,"Ambos")</f>
+        <f>COUNTIFS('S1'!$B$6:$B$32,$A35,'S1'!$E$6:$E$32,"Diego")+COUNTIFS('S1'!$B$6:$B$32,$A35,'S1'!$E$6:$E$32,"Ambos")+COUNTIFS('S2'!$B$6:$B$23,$A35,'S2'!$E$6:$E$23,"Diego")+COUNTIFS('S2'!$B$6:$B$23,$A35,'S2'!$E$6:$E$23,"Ambos")+COUNTIFS('S3'!$B$6:$B$24,$A35,'S3'!$E$6:$E$24,"Diego")+COUNTIFS('S3'!$B$6:$B$24,$A35,'S3'!$E$6:$E$24,"Ambos")+COUNTIFS('S4'!$B$6:$B$22,$A35,'S4'!$E$6:$E$22,"Diego")+COUNTIFS('S4'!$B$6:$B$22,$A35,'S4'!$E$6:$E$22,"Ambos")+COUNTIFS('S5'!$B$6:$B$20,$A35,'S5'!$E$6:$E$20,"Diego")+COUNTIFS('S5'!$B$6:$B$20,$A35,'S5'!$E$6:$E$20,"Ambos")+COUNTIFS('S6'!$B$6:$B$17,$A35,'S6'!$E$6:$E$17,"Diego")+COUNTIFS('S6'!$B$6:$B$17,$A35,'S6'!$E$6:$E$17,"Ambos")+COUNTIFS('S7'!$B$6:$B$19,$A35,'S7'!$E$6:$E$19,"Diego")+COUNTIFS('S7'!$B$6:$B$19,$A35,'S7'!$E$6:$E$19,"Ambos")+COUNTIFS('S8'!$B$6:$B$23,$A35,'S8'!$E$6:$E$23,"Diego")+COUNTIFS('S8'!$B$6:$B$23,$A35,'S8'!$E$6:$E$23,"Ambos")+COUNTIFS('S9'!$B$6:$B$15,$A35,'S9'!$E$6:$E$15,"Diego")+COUNTIFS('S9'!$B$6:$B$15,$A35,'S9'!$E$6:$E$15,"Ambos")+COUNTIFS('S10'!$B$6:$B$13,$A35,'S10'!$E$6:$E$13,"Diego")+COUNTIFS('S10'!$B$6:$B$13,$A35,'S10'!$E$6:$E$13,"Ambos")+COUNTIFS('Holgura'!$B$6:$B$11,$A35,'Holgura'!$E$6:$E$11,"Diego")+COUNTIFS('Holgura'!$B$6:$B$11,$A35,'Holgura'!$E$6:$E$11,"Ambos")+COUNTIFS('Entrega'!$B$6:$B$9,$A35,'Entrega'!$E$6:$E$9,"Diego")+COUNTIFS('Entrega'!$B$6:$B$9,$A35,'Entrega'!$E$6:$E$9,"Ambos")+COUNTIFS('Defensa'!$B$6:$B$10,$A35,'Defensa'!$E$6:$E$10,"Diego")+COUNTIFS('Defensa'!$B$6:$B$10,$A35,'Defensa'!$E$6:$E$10,"Ambos")</f>
         <v/>
       </c>
     </row>
@@ -9579,19 +9600,19 @@
         <v/>
       </c>
       <c r="D36" s="21">
-        <f>SUMIFS('S1'!$I$6:$I$32,'S1'!$B$6:$B$32,$A36,'S1'!$E$6:$E$32,"Víctor")+SUMIFS('S1'!$I$6:$I$32,'S1'!$B$6:$B$32,$A36,'S1'!$E$6:$E$32,"Ambos")+SUMIFS('S2'!$I$6:$I$23,'S2'!$B$6:$B$23,$A36,'S2'!$E$6:$E$23,"Víctor")+SUMIFS('S2'!$I$6:$I$23,'S2'!$B$6:$B$23,$A36,'S2'!$E$6:$E$23,"Ambos")+SUMIFS('S3'!$I$6:$I$19,'S3'!$B$6:$B$19,$A36,'S3'!$E$6:$E$19,"Víctor")+SUMIFS('S3'!$I$6:$I$19,'S3'!$B$6:$B$19,$A36,'S3'!$E$6:$E$19,"Ambos")+SUMIFS('S4'!$I$6:$I$20,'S4'!$B$6:$B$20,$A36,'S4'!$E$6:$E$20,"Víctor")+SUMIFS('S4'!$I$6:$I$20,'S4'!$B$6:$B$20,$A36,'S4'!$E$6:$E$20,"Ambos")+SUMIFS('S5'!$I$6:$I$20,'S5'!$B$6:$B$20,$A36,'S5'!$E$6:$E$20,"Víctor")+SUMIFS('S5'!$I$6:$I$20,'S5'!$B$6:$B$20,$A36,'S5'!$E$6:$E$20,"Ambos")+SUMIFS('S6'!$I$6:$I$17,'S6'!$B$6:$B$17,$A36,'S6'!$E$6:$E$17,"Víctor")+SUMIFS('S6'!$I$6:$I$17,'S6'!$B$6:$B$17,$A36,'S6'!$E$6:$E$17,"Ambos")+SUMIFS('S7'!$I$6:$I$19,'S7'!$B$6:$B$19,$A36,'S7'!$E$6:$E$19,"Víctor")+SUMIFS('S7'!$I$6:$I$19,'S7'!$B$6:$B$19,$A36,'S7'!$E$6:$E$19,"Ambos")+SUMIFS('S8'!$I$6:$I$23,'S8'!$B$6:$B$23,$A36,'S8'!$E$6:$E$23,"Víctor")+SUMIFS('S8'!$I$6:$I$23,'S8'!$B$6:$B$23,$A36,'S8'!$E$6:$E$23,"Ambos")+SUMIFS('S9'!$I$6:$I$15,'S9'!$B$6:$B$15,$A36,'S9'!$E$6:$E$15,"Víctor")+SUMIFS('S9'!$I$6:$I$15,'S9'!$B$6:$B$15,$A36,'S9'!$E$6:$E$15,"Ambos")+SUMIFS('S10'!$I$6:$I$13,'S10'!$B$6:$B$13,$A36,'S10'!$E$6:$E$13,"Víctor")+SUMIFS('S10'!$I$6:$I$13,'S10'!$B$6:$B$13,$A36,'S10'!$E$6:$E$13,"Ambos")+SUMIFS('Holgura'!$I$6:$I$11,'Holgura'!$B$6:$B$11,$A36,'Holgura'!$E$6:$E$11,"Víctor")+SUMIFS('Holgura'!$I$6:$I$11,'Holgura'!$B$6:$B$11,$A36,'Holgura'!$E$6:$E$11,"Ambos")+SUMIFS('Entrega'!$I$6:$I$9,'Entrega'!$B$6:$B$9,$A36,'Entrega'!$E$6:$E$9,"Víctor")+SUMIFS('Entrega'!$I$6:$I$9,'Entrega'!$B$6:$B$9,$A36,'Entrega'!$E$6:$E$9,"Ambos")+SUMIFS('Defensa'!$I$6:$I$10,'Defensa'!$B$6:$B$10,$A36,'Defensa'!$E$6:$E$10,"Víctor")+SUMIFS('Defensa'!$I$6:$I$10,'Defensa'!$B$6:$B$10,$A36,'Defensa'!$E$6:$E$10,"Ambos")</f>
+        <f>SUMIFS('S1'!$I$6:$I$32,'S1'!$B$6:$B$32,$A36,'S1'!$E$6:$E$32,"Víctor")+SUMIFS('S1'!$I$6:$I$32,'S1'!$B$6:$B$32,$A36,'S1'!$E$6:$E$32,"Ambos")+SUMIFS('S2'!$I$6:$I$23,'S2'!$B$6:$B$23,$A36,'S2'!$E$6:$E$23,"Víctor")+SUMIFS('S2'!$I$6:$I$23,'S2'!$B$6:$B$23,$A36,'S2'!$E$6:$E$23,"Ambos")+SUMIFS('S3'!$I$6:$I$24,'S3'!$B$6:$B$24,$A36,'S3'!$E$6:$E$24,"Víctor")+SUMIFS('S3'!$I$6:$I$24,'S3'!$B$6:$B$24,$A36,'S3'!$E$6:$E$24,"Ambos")+SUMIFS('S4'!$I$6:$I$22,'S4'!$B$6:$B$22,$A36,'S4'!$E$6:$E$22,"Víctor")+SUMIFS('S4'!$I$6:$I$22,'S4'!$B$6:$B$22,$A36,'S4'!$E$6:$E$22,"Ambos")+SUMIFS('S5'!$I$6:$I$20,'S5'!$B$6:$B$20,$A36,'S5'!$E$6:$E$20,"Víctor")+SUMIFS('S5'!$I$6:$I$20,'S5'!$B$6:$B$20,$A36,'S5'!$E$6:$E$20,"Ambos")+SUMIFS('S6'!$I$6:$I$17,'S6'!$B$6:$B$17,$A36,'S6'!$E$6:$E$17,"Víctor")+SUMIFS('S6'!$I$6:$I$17,'S6'!$B$6:$B$17,$A36,'S6'!$E$6:$E$17,"Ambos")+SUMIFS('S7'!$I$6:$I$19,'S7'!$B$6:$B$19,$A36,'S7'!$E$6:$E$19,"Víctor")+SUMIFS('S7'!$I$6:$I$19,'S7'!$B$6:$B$19,$A36,'S7'!$E$6:$E$19,"Ambos")+SUMIFS('S8'!$I$6:$I$23,'S8'!$B$6:$B$23,$A36,'S8'!$E$6:$E$23,"Víctor")+SUMIFS('S8'!$I$6:$I$23,'S8'!$B$6:$B$23,$A36,'S8'!$E$6:$E$23,"Ambos")+SUMIFS('S9'!$I$6:$I$15,'S9'!$B$6:$B$15,$A36,'S9'!$E$6:$E$15,"Víctor")+SUMIFS('S9'!$I$6:$I$15,'S9'!$B$6:$B$15,$A36,'S9'!$E$6:$E$15,"Ambos")+SUMIFS('S10'!$I$6:$I$13,'S10'!$B$6:$B$13,$A36,'S10'!$E$6:$E$13,"Víctor")+SUMIFS('S10'!$I$6:$I$13,'S10'!$B$6:$B$13,$A36,'S10'!$E$6:$E$13,"Ambos")+SUMIFS('Holgura'!$I$6:$I$11,'Holgura'!$B$6:$B$11,$A36,'Holgura'!$E$6:$E$11,"Víctor")+SUMIFS('Holgura'!$I$6:$I$11,'Holgura'!$B$6:$B$11,$A36,'Holgura'!$E$6:$E$11,"Ambos")+SUMIFS('Entrega'!$I$6:$I$9,'Entrega'!$B$6:$B$9,$A36,'Entrega'!$E$6:$E$9,"Víctor")+SUMIFS('Entrega'!$I$6:$I$9,'Entrega'!$B$6:$B$9,$A36,'Entrega'!$E$6:$E$9,"Ambos")+SUMIFS('Defensa'!$I$6:$I$10,'Defensa'!$B$6:$B$10,$A36,'Defensa'!$E$6:$E$10,"Víctor")+SUMIFS('Defensa'!$I$6:$I$10,'Defensa'!$B$6:$B$10,$A36,'Defensa'!$E$6:$E$10,"Ambos")</f>
         <v/>
       </c>
       <c r="E36" s="21">
-        <f>SUMIFS('S1'!$I$6:$I$32,'S1'!$B$6:$B$32,$A36,'S1'!$E$6:$E$32,"Diego")+SUMIFS('S1'!$I$6:$I$32,'S1'!$B$6:$B$32,$A36,'S1'!$E$6:$E$32,"Ambos")+SUMIFS('S2'!$I$6:$I$23,'S2'!$B$6:$B$23,$A36,'S2'!$E$6:$E$23,"Diego")+SUMIFS('S2'!$I$6:$I$23,'S2'!$B$6:$B$23,$A36,'S2'!$E$6:$E$23,"Ambos")+SUMIFS('S3'!$I$6:$I$19,'S3'!$B$6:$B$19,$A36,'S3'!$E$6:$E$19,"Diego")+SUMIFS('S3'!$I$6:$I$19,'S3'!$B$6:$B$19,$A36,'S3'!$E$6:$E$19,"Ambos")+SUMIFS('S4'!$I$6:$I$20,'S4'!$B$6:$B$20,$A36,'S4'!$E$6:$E$20,"Diego")+SUMIFS('S4'!$I$6:$I$20,'S4'!$B$6:$B$20,$A36,'S4'!$E$6:$E$20,"Ambos")+SUMIFS('S5'!$I$6:$I$20,'S5'!$B$6:$B$20,$A36,'S5'!$E$6:$E$20,"Diego")+SUMIFS('S5'!$I$6:$I$20,'S5'!$B$6:$B$20,$A36,'S5'!$E$6:$E$20,"Ambos")+SUMIFS('S6'!$I$6:$I$17,'S6'!$B$6:$B$17,$A36,'S6'!$E$6:$E$17,"Diego")+SUMIFS('S6'!$I$6:$I$17,'S6'!$B$6:$B$17,$A36,'S6'!$E$6:$E$17,"Ambos")+SUMIFS('S7'!$I$6:$I$19,'S7'!$B$6:$B$19,$A36,'S7'!$E$6:$E$19,"Diego")+SUMIFS('S7'!$I$6:$I$19,'S7'!$B$6:$B$19,$A36,'S7'!$E$6:$E$19,"Ambos")+SUMIFS('S8'!$I$6:$I$23,'S8'!$B$6:$B$23,$A36,'S8'!$E$6:$E$23,"Diego")+SUMIFS('S8'!$I$6:$I$23,'S8'!$B$6:$B$23,$A36,'S8'!$E$6:$E$23,"Ambos")+SUMIFS('S9'!$I$6:$I$15,'S9'!$B$6:$B$15,$A36,'S9'!$E$6:$E$15,"Diego")+SUMIFS('S9'!$I$6:$I$15,'S9'!$B$6:$B$15,$A36,'S9'!$E$6:$E$15,"Ambos")+SUMIFS('S10'!$I$6:$I$13,'S10'!$B$6:$B$13,$A36,'S10'!$E$6:$E$13,"Diego")+SUMIFS('S10'!$I$6:$I$13,'S10'!$B$6:$B$13,$A36,'S10'!$E$6:$E$13,"Ambos")+SUMIFS('Holgura'!$I$6:$I$11,'Holgura'!$B$6:$B$11,$A36,'Holgura'!$E$6:$E$11,"Diego")+SUMIFS('Holgura'!$I$6:$I$11,'Holgura'!$B$6:$B$11,$A36,'Holgura'!$E$6:$E$11,"Ambos")+SUMIFS('Entrega'!$I$6:$I$9,'Entrega'!$B$6:$B$9,$A36,'Entrega'!$E$6:$E$9,"Diego")+SUMIFS('Entrega'!$I$6:$I$9,'Entrega'!$B$6:$B$9,$A36,'Entrega'!$E$6:$E$9,"Ambos")+SUMIFS('Defensa'!$I$6:$I$10,'Defensa'!$B$6:$B$10,$A36,'Defensa'!$E$6:$E$10,"Diego")+SUMIFS('Defensa'!$I$6:$I$10,'Defensa'!$B$6:$B$10,$A36,'Defensa'!$E$6:$E$10,"Ambos")</f>
+        <f>SUMIFS('S1'!$I$6:$I$32,'S1'!$B$6:$B$32,$A36,'S1'!$E$6:$E$32,"Diego")+SUMIFS('S1'!$I$6:$I$32,'S1'!$B$6:$B$32,$A36,'S1'!$E$6:$E$32,"Ambos")+SUMIFS('S2'!$I$6:$I$23,'S2'!$B$6:$B$23,$A36,'S2'!$E$6:$E$23,"Diego")+SUMIFS('S2'!$I$6:$I$23,'S2'!$B$6:$B$23,$A36,'S2'!$E$6:$E$23,"Ambos")+SUMIFS('S3'!$I$6:$I$24,'S3'!$B$6:$B$24,$A36,'S3'!$E$6:$E$24,"Diego")+SUMIFS('S3'!$I$6:$I$24,'S3'!$B$6:$B$24,$A36,'S3'!$E$6:$E$24,"Ambos")+SUMIFS('S4'!$I$6:$I$22,'S4'!$B$6:$B$22,$A36,'S4'!$E$6:$E$22,"Diego")+SUMIFS('S4'!$I$6:$I$22,'S4'!$B$6:$B$22,$A36,'S4'!$E$6:$E$22,"Ambos")+SUMIFS('S5'!$I$6:$I$20,'S5'!$B$6:$B$20,$A36,'S5'!$E$6:$E$20,"Diego")+SUMIFS('S5'!$I$6:$I$20,'S5'!$B$6:$B$20,$A36,'S5'!$E$6:$E$20,"Ambos")+SUMIFS('S6'!$I$6:$I$17,'S6'!$B$6:$B$17,$A36,'S6'!$E$6:$E$17,"Diego")+SUMIFS('S6'!$I$6:$I$17,'S6'!$B$6:$B$17,$A36,'S6'!$E$6:$E$17,"Ambos")+SUMIFS('S7'!$I$6:$I$19,'S7'!$B$6:$B$19,$A36,'S7'!$E$6:$E$19,"Diego")+SUMIFS('S7'!$I$6:$I$19,'S7'!$B$6:$B$19,$A36,'S7'!$E$6:$E$19,"Ambos")+SUMIFS('S8'!$I$6:$I$23,'S8'!$B$6:$B$23,$A36,'S8'!$E$6:$E$23,"Diego")+SUMIFS('S8'!$I$6:$I$23,'S8'!$B$6:$B$23,$A36,'S8'!$E$6:$E$23,"Ambos")+SUMIFS('S9'!$I$6:$I$15,'S9'!$B$6:$B$15,$A36,'S9'!$E$6:$E$15,"Diego")+SUMIFS('S9'!$I$6:$I$15,'S9'!$B$6:$B$15,$A36,'S9'!$E$6:$E$15,"Ambos")+SUMIFS('S10'!$I$6:$I$13,'S10'!$B$6:$B$13,$A36,'S10'!$E$6:$E$13,"Diego")+SUMIFS('S10'!$I$6:$I$13,'S10'!$B$6:$B$13,$A36,'S10'!$E$6:$E$13,"Ambos")+SUMIFS('Holgura'!$I$6:$I$11,'Holgura'!$B$6:$B$11,$A36,'Holgura'!$E$6:$E$11,"Diego")+SUMIFS('Holgura'!$I$6:$I$11,'Holgura'!$B$6:$B$11,$A36,'Holgura'!$E$6:$E$11,"Ambos")+SUMIFS('Entrega'!$I$6:$I$9,'Entrega'!$B$6:$B$9,$A36,'Entrega'!$E$6:$E$9,"Diego")+SUMIFS('Entrega'!$I$6:$I$9,'Entrega'!$B$6:$B$9,$A36,'Entrega'!$E$6:$E$9,"Ambos")+SUMIFS('Defensa'!$I$6:$I$10,'Defensa'!$B$6:$B$10,$A36,'Defensa'!$E$6:$E$10,"Diego")+SUMIFS('Defensa'!$I$6:$I$10,'Defensa'!$B$6:$B$10,$A36,'Defensa'!$E$6:$E$10,"Ambos")</f>
         <v/>
       </c>
       <c r="F36" s="21">
-        <f>COUNTIFS('S1'!$B$6:$B$32,$A36,'S1'!$E$6:$E$32,"Víctor")+COUNTIFS('S1'!$B$6:$B$32,$A36,'S1'!$E$6:$E$32,"Ambos")+COUNTIFS('S2'!$B$6:$B$23,$A36,'S2'!$E$6:$E$23,"Víctor")+COUNTIFS('S2'!$B$6:$B$23,$A36,'S2'!$E$6:$E$23,"Ambos")+COUNTIFS('S3'!$B$6:$B$19,$A36,'S3'!$E$6:$E$19,"Víctor")+COUNTIFS('S3'!$B$6:$B$19,$A36,'S3'!$E$6:$E$19,"Ambos")+COUNTIFS('S4'!$B$6:$B$20,$A36,'S4'!$E$6:$E$20,"Víctor")+COUNTIFS('S4'!$B$6:$B$20,$A36,'S4'!$E$6:$E$20,"Ambos")+COUNTIFS('S5'!$B$6:$B$20,$A36,'S5'!$E$6:$E$20,"Víctor")+COUNTIFS('S5'!$B$6:$B$20,$A36,'S5'!$E$6:$E$20,"Ambos")+COUNTIFS('S6'!$B$6:$B$17,$A36,'S6'!$E$6:$E$17,"Víctor")+COUNTIFS('S6'!$B$6:$B$17,$A36,'S6'!$E$6:$E$17,"Ambos")+COUNTIFS('S7'!$B$6:$B$19,$A36,'S7'!$E$6:$E$19,"Víctor")+COUNTIFS('S7'!$B$6:$B$19,$A36,'S7'!$E$6:$E$19,"Ambos")+COUNTIFS('S8'!$B$6:$B$23,$A36,'S8'!$E$6:$E$23,"Víctor")+COUNTIFS('S8'!$B$6:$B$23,$A36,'S8'!$E$6:$E$23,"Ambos")+COUNTIFS('S9'!$B$6:$B$15,$A36,'S9'!$E$6:$E$15,"Víctor")+COUNTIFS('S9'!$B$6:$B$15,$A36,'S9'!$E$6:$E$15,"Ambos")+COUNTIFS('S10'!$B$6:$B$13,$A36,'S10'!$E$6:$E$13,"Víctor")+COUNTIFS('S10'!$B$6:$B$13,$A36,'S10'!$E$6:$E$13,"Ambos")+COUNTIFS('Holgura'!$B$6:$B$11,$A36,'Holgura'!$E$6:$E$11,"Víctor")+COUNTIFS('Holgura'!$B$6:$B$11,$A36,'Holgura'!$E$6:$E$11,"Ambos")+COUNTIFS('Entrega'!$B$6:$B$9,$A36,'Entrega'!$E$6:$E$9,"Víctor")+COUNTIFS('Entrega'!$B$6:$B$9,$A36,'Entrega'!$E$6:$E$9,"Ambos")+COUNTIFS('Defensa'!$B$6:$B$10,$A36,'Defensa'!$E$6:$E$10,"Víctor")+COUNTIFS('Defensa'!$B$6:$B$10,$A36,'Defensa'!$E$6:$E$10,"Ambos")</f>
+        <f>COUNTIFS('S1'!$B$6:$B$32,$A36,'S1'!$E$6:$E$32,"Víctor")+COUNTIFS('S1'!$B$6:$B$32,$A36,'S1'!$E$6:$E$32,"Ambos")+COUNTIFS('S2'!$B$6:$B$23,$A36,'S2'!$E$6:$E$23,"Víctor")+COUNTIFS('S2'!$B$6:$B$23,$A36,'S2'!$E$6:$E$23,"Ambos")+COUNTIFS('S3'!$B$6:$B$24,$A36,'S3'!$E$6:$E$24,"Víctor")+COUNTIFS('S3'!$B$6:$B$24,$A36,'S3'!$E$6:$E$24,"Ambos")+COUNTIFS('S4'!$B$6:$B$22,$A36,'S4'!$E$6:$E$22,"Víctor")+COUNTIFS('S4'!$B$6:$B$22,$A36,'S4'!$E$6:$E$22,"Ambos")+COUNTIFS('S5'!$B$6:$B$20,$A36,'S5'!$E$6:$E$20,"Víctor")+COUNTIFS('S5'!$B$6:$B$20,$A36,'S5'!$E$6:$E$20,"Ambos")+COUNTIFS('S6'!$B$6:$B$17,$A36,'S6'!$E$6:$E$17,"Víctor")+COUNTIFS('S6'!$B$6:$B$17,$A36,'S6'!$E$6:$E$17,"Ambos")+COUNTIFS('S7'!$B$6:$B$19,$A36,'S7'!$E$6:$E$19,"Víctor")+COUNTIFS('S7'!$B$6:$B$19,$A36,'S7'!$E$6:$E$19,"Ambos")+COUNTIFS('S8'!$B$6:$B$23,$A36,'S8'!$E$6:$E$23,"Víctor")+COUNTIFS('S8'!$B$6:$B$23,$A36,'S8'!$E$6:$E$23,"Ambos")+COUNTIFS('S9'!$B$6:$B$15,$A36,'S9'!$E$6:$E$15,"Víctor")+COUNTIFS('S9'!$B$6:$B$15,$A36,'S9'!$E$6:$E$15,"Ambos")+COUNTIFS('S10'!$B$6:$B$13,$A36,'S10'!$E$6:$E$13,"Víctor")+COUNTIFS('S10'!$B$6:$B$13,$A36,'S10'!$E$6:$E$13,"Ambos")+COUNTIFS('Holgura'!$B$6:$B$11,$A36,'Holgura'!$E$6:$E$11,"Víctor")+COUNTIFS('Holgura'!$B$6:$B$11,$A36,'Holgura'!$E$6:$E$11,"Ambos")+COUNTIFS('Entrega'!$B$6:$B$9,$A36,'Entrega'!$E$6:$E$9,"Víctor")+COUNTIFS('Entrega'!$B$6:$B$9,$A36,'Entrega'!$E$6:$E$9,"Ambos")+COUNTIFS('Defensa'!$B$6:$B$10,$A36,'Defensa'!$E$6:$E$10,"Víctor")+COUNTIFS('Defensa'!$B$6:$B$10,$A36,'Defensa'!$E$6:$E$10,"Ambos")</f>
         <v/>
       </c>
       <c r="G36" s="21">
-        <f>COUNTIFS('S1'!$B$6:$B$32,$A36,'S1'!$E$6:$E$32,"Diego")+COUNTIFS('S1'!$B$6:$B$32,$A36,'S1'!$E$6:$E$32,"Ambos")+COUNTIFS('S2'!$B$6:$B$23,$A36,'S2'!$E$6:$E$23,"Diego")+COUNTIFS('S2'!$B$6:$B$23,$A36,'S2'!$E$6:$E$23,"Ambos")+COUNTIFS('S3'!$B$6:$B$19,$A36,'S3'!$E$6:$E$19,"Diego")+COUNTIFS('S3'!$B$6:$B$19,$A36,'S3'!$E$6:$E$19,"Ambos")+COUNTIFS('S4'!$B$6:$B$20,$A36,'S4'!$E$6:$E$20,"Diego")+COUNTIFS('S4'!$B$6:$B$20,$A36,'S4'!$E$6:$E$20,"Ambos")+COUNTIFS('S5'!$B$6:$B$20,$A36,'S5'!$E$6:$E$20,"Diego")+COUNTIFS('S5'!$B$6:$B$20,$A36,'S5'!$E$6:$E$20,"Ambos")+COUNTIFS('S6'!$B$6:$B$17,$A36,'S6'!$E$6:$E$17,"Diego")+COUNTIFS('S6'!$B$6:$B$17,$A36,'S6'!$E$6:$E$17,"Ambos")+COUNTIFS('S7'!$B$6:$B$19,$A36,'S7'!$E$6:$E$19,"Diego")+COUNTIFS('S7'!$B$6:$B$19,$A36,'S7'!$E$6:$E$19,"Ambos")+COUNTIFS('S8'!$B$6:$B$23,$A36,'S8'!$E$6:$E$23,"Diego")+COUNTIFS('S8'!$B$6:$B$23,$A36,'S8'!$E$6:$E$23,"Ambos")+COUNTIFS('S9'!$B$6:$B$15,$A36,'S9'!$E$6:$E$15,"Diego")+COUNTIFS('S9'!$B$6:$B$15,$A36,'S9'!$E$6:$E$15,"Ambos")+COUNTIFS('S10'!$B$6:$B$13,$A36,'S10'!$E$6:$E$13,"Diego")+COUNTIFS('S10'!$B$6:$B$13,$A36,'S10'!$E$6:$E$13,"Ambos")+COUNTIFS('Holgura'!$B$6:$B$11,$A36,'Holgura'!$E$6:$E$11,"Diego")+COUNTIFS('Holgura'!$B$6:$B$11,$A36,'Holgura'!$E$6:$E$11,"Ambos")+COUNTIFS('Entrega'!$B$6:$B$9,$A36,'Entrega'!$E$6:$E$9,"Diego")+COUNTIFS('Entrega'!$B$6:$B$9,$A36,'Entrega'!$E$6:$E$9,"Ambos")+COUNTIFS('Defensa'!$B$6:$B$10,$A36,'Defensa'!$E$6:$E$10,"Diego")+COUNTIFS('Defensa'!$B$6:$B$10,$A36,'Defensa'!$E$6:$E$10,"Ambos")</f>
+        <f>COUNTIFS('S1'!$B$6:$B$32,$A36,'S1'!$E$6:$E$32,"Diego")+COUNTIFS('S1'!$B$6:$B$32,$A36,'S1'!$E$6:$E$32,"Ambos")+COUNTIFS('S2'!$B$6:$B$23,$A36,'S2'!$E$6:$E$23,"Diego")+COUNTIFS('S2'!$B$6:$B$23,$A36,'S2'!$E$6:$E$23,"Ambos")+COUNTIFS('S3'!$B$6:$B$24,$A36,'S3'!$E$6:$E$24,"Diego")+COUNTIFS('S3'!$B$6:$B$24,$A36,'S3'!$E$6:$E$24,"Ambos")+COUNTIFS('S4'!$B$6:$B$22,$A36,'S4'!$E$6:$E$22,"Diego")+COUNTIFS('S4'!$B$6:$B$22,$A36,'S4'!$E$6:$E$22,"Ambos")+COUNTIFS('S5'!$B$6:$B$20,$A36,'S5'!$E$6:$E$20,"Diego")+COUNTIFS('S5'!$B$6:$B$20,$A36,'S5'!$E$6:$E$20,"Ambos")+COUNTIFS('S6'!$B$6:$B$17,$A36,'S6'!$E$6:$E$17,"Diego")+COUNTIFS('S6'!$B$6:$B$17,$A36,'S6'!$E$6:$E$17,"Ambos")+COUNTIFS('S7'!$B$6:$B$19,$A36,'S7'!$E$6:$E$19,"Diego")+COUNTIFS('S7'!$B$6:$B$19,$A36,'S7'!$E$6:$E$19,"Ambos")+COUNTIFS('S8'!$B$6:$B$23,$A36,'S8'!$E$6:$E$23,"Diego")+COUNTIFS('S8'!$B$6:$B$23,$A36,'S8'!$E$6:$E$23,"Ambos")+COUNTIFS('S9'!$B$6:$B$15,$A36,'S9'!$E$6:$E$15,"Diego")+COUNTIFS('S9'!$B$6:$B$15,$A36,'S9'!$E$6:$E$15,"Ambos")+COUNTIFS('S10'!$B$6:$B$13,$A36,'S10'!$E$6:$E$13,"Diego")+COUNTIFS('S10'!$B$6:$B$13,$A36,'S10'!$E$6:$E$13,"Ambos")+COUNTIFS('Holgura'!$B$6:$B$11,$A36,'Holgura'!$E$6:$E$11,"Diego")+COUNTIFS('Holgura'!$B$6:$B$11,$A36,'Holgura'!$E$6:$E$11,"Ambos")+COUNTIFS('Entrega'!$B$6:$B$9,$A36,'Entrega'!$E$6:$E$9,"Diego")+COUNTIFS('Entrega'!$B$6:$B$9,$A36,'Entrega'!$E$6:$E$9,"Ambos")+COUNTIFS('Defensa'!$B$6:$B$10,$A36,'Defensa'!$E$6:$E$10,"Diego")+COUNTIFS('Defensa'!$B$6:$B$10,$A36,'Defensa'!$E$6:$E$10,"Ambos")</f>
         <v/>
       </c>
     </row>
@@ -9608,19 +9629,19 @@
         <v/>
       </c>
       <c r="D37" s="21">
-        <f>SUMIFS('S1'!$I$6:$I$32,'S1'!$B$6:$B$32,$A37,'S1'!$E$6:$E$32,"Víctor")+SUMIFS('S1'!$I$6:$I$32,'S1'!$B$6:$B$32,$A37,'S1'!$E$6:$E$32,"Ambos")+SUMIFS('S2'!$I$6:$I$23,'S2'!$B$6:$B$23,$A37,'S2'!$E$6:$E$23,"Víctor")+SUMIFS('S2'!$I$6:$I$23,'S2'!$B$6:$B$23,$A37,'S2'!$E$6:$E$23,"Ambos")+SUMIFS('S3'!$I$6:$I$19,'S3'!$B$6:$B$19,$A37,'S3'!$E$6:$E$19,"Víctor")+SUMIFS('S3'!$I$6:$I$19,'S3'!$B$6:$B$19,$A37,'S3'!$E$6:$E$19,"Ambos")+SUMIFS('S4'!$I$6:$I$20,'S4'!$B$6:$B$20,$A37,'S4'!$E$6:$E$20,"Víctor")+SUMIFS('S4'!$I$6:$I$20,'S4'!$B$6:$B$20,$A37,'S4'!$E$6:$E$20,"Ambos")+SUMIFS('S5'!$I$6:$I$20,'S5'!$B$6:$B$20,$A37,'S5'!$E$6:$E$20,"Víctor")+SUMIFS('S5'!$I$6:$I$20,'S5'!$B$6:$B$20,$A37,'S5'!$E$6:$E$20,"Ambos")+SUMIFS('S6'!$I$6:$I$17,'S6'!$B$6:$B$17,$A37,'S6'!$E$6:$E$17,"Víctor")+SUMIFS('S6'!$I$6:$I$17,'S6'!$B$6:$B$17,$A37,'S6'!$E$6:$E$17,"Ambos")+SUMIFS('S7'!$I$6:$I$19,'S7'!$B$6:$B$19,$A37,'S7'!$E$6:$E$19,"Víctor")+SUMIFS('S7'!$I$6:$I$19,'S7'!$B$6:$B$19,$A37,'S7'!$E$6:$E$19,"Ambos")+SUMIFS('S8'!$I$6:$I$23,'S8'!$B$6:$B$23,$A37,'S8'!$E$6:$E$23,"Víctor")+SUMIFS('S8'!$I$6:$I$23,'S8'!$B$6:$B$23,$A37,'S8'!$E$6:$E$23,"Ambos")+SUMIFS('S9'!$I$6:$I$15,'S9'!$B$6:$B$15,$A37,'S9'!$E$6:$E$15,"Víctor")+SUMIFS('S9'!$I$6:$I$15,'S9'!$B$6:$B$15,$A37,'S9'!$E$6:$E$15,"Ambos")+SUMIFS('S10'!$I$6:$I$13,'S10'!$B$6:$B$13,$A37,'S10'!$E$6:$E$13,"Víctor")+SUMIFS('S10'!$I$6:$I$13,'S10'!$B$6:$B$13,$A37,'S10'!$E$6:$E$13,"Ambos")+SUMIFS('Holgura'!$I$6:$I$11,'Holgura'!$B$6:$B$11,$A37,'Holgura'!$E$6:$E$11,"Víctor")+SUMIFS('Holgura'!$I$6:$I$11,'Holgura'!$B$6:$B$11,$A37,'Holgura'!$E$6:$E$11,"Ambos")+SUMIFS('Entrega'!$I$6:$I$9,'Entrega'!$B$6:$B$9,$A37,'Entrega'!$E$6:$E$9,"Víctor")+SUMIFS('Entrega'!$I$6:$I$9,'Entrega'!$B$6:$B$9,$A37,'Entrega'!$E$6:$E$9,"Ambos")+SUMIFS('Defensa'!$I$6:$I$10,'Defensa'!$B$6:$B$10,$A37,'Defensa'!$E$6:$E$10,"Víctor")+SUMIFS('Defensa'!$I$6:$I$10,'Defensa'!$B$6:$B$10,$A37,'Defensa'!$E$6:$E$10,"Ambos")</f>
+        <f>SUMIFS('S1'!$I$6:$I$32,'S1'!$B$6:$B$32,$A37,'S1'!$E$6:$E$32,"Víctor")+SUMIFS('S1'!$I$6:$I$32,'S1'!$B$6:$B$32,$A37,'S1'!$E$6:$E$32,"Ambos")+SUMIFS('S2'!$I$6:$I$23,'S2'!$B$6:$B$23,$A37,'S2'!$E$6:$E$23,"Víctor")+SUMIFS('S2'!$I$6:$I$23,'S2'!$B$6:$B$23,$A37,'S2'!$E$6:$E$23,"Ambos")+SUMIFS('S3'!$I$6:$I$24,'S3'!$B$6:$B$24,$A37,'S3'!$E$6:$E$24,"Víctor")+SUMIFS('S3'!$I$6:$I$24,'S3'!$B$6:$B$24,$A37,'S3'!$E$6:$E$24,"Ambos")+SUMIFS('S4'!$I$6:$I$22,'S4'!$B$6:$B$22,$A37,'S4'!$E$6:$E$22,"Víctor")+SUMIFS('S4'!$I$6:$I$22,'S4'!$B$6:$B$22,$A37,'S4'!$E$6:$E$22,"Ambos")+SUMIFS('S5'!$I$6:$I$20,'S5'!$B$6:$B$20,$A37,'S5'!$E$6:$E$20,"Víctor")+SUMIFS('S5'!$I$6:$I$20,'S5'!$B$6:$B$20,$A37,'S5'!$E$6:$E$20,"Ambos")+SUMIFS('S6'!$I$6:$I$17,'S6'!$B$6:$B$17,$A37,'S6'!$E$6:$E$17,"Víctor")+SUMIFS('S6'!$I$6:$I$17,'S6'!$B$6:$B$17,$A37,'S6'!$E$6:$E$17,"Ambos")+SUMIFS('S7'!$I$6:$I$19,'S7'!$B$6:$B$19,$A37,'S7'!$E$6:$E$19,"Víctor")+SUMIFS('S7'!$I$6:$I$19,'S7'!$B$6:$B$19,$A37,'S7'!$E$6:$E$19,"Ambos")+SUMIFS('S8'!$I$6:$I$23,'S8'!$B$6:$B$23,$A37,'S8'!$E$6:$E$23,"Víctor")+SUMIFS('S8'!$I$6:$I$23,'S8'!$B$6:$B$23,$A37,'S8'!$E$6:$E$23,"Ambos")+SUMIFS('S9'!$I$6:$I$15,'S9'!$B$6:$B$15,$A37,'S9'!$E$6:$E$15,"Víctor")+SUMIFS('S9'!$I$6:$I$15,'S9'!$B$6:$B$15,$A37,'S9'!$E$6:$E$15,"Ambos")+SUMIFS('S10'!$I$6:$I$13,'S10'!$B$6:$B$13,$A37,'S10'!$E$6:$E$13,"Víctor")+SUMIFS('S10'!$I$6:$I$13,'S10'!$B$6:$B$13,$A37,'S10'!$E$6:$E$13,"Ambos")+SUMIFS('Holgura'!$I$6:$I$11,'Holgura'!$B$6:$B$11,$A37,'Holgura'!$E$6:$E$11,"Víctor")+SUMIFS('Holgura'!$I$6:$I$11,'Holgura'!$B$6:$B$11,$A37,'Holgura'!$E$6:$E$11,"Ambos")+SUMIFS('Entrega'!$I$6:$I$9,'Entrega'!$B$6:$B$9,$A37,'Entrega'!$E$6:$E$9,"Víctor")+SUMIFS('Entrega'!$I$6:$I$9,'Entrega'!$B$6:$B$9,$A37,'Entrega'!$E$6:$E$9,"Ambos")+SUMIFS('Defensa'!$I$6:$I$10,'Defensa'!$B$6:$B$10,$A37,'Defensa'!$E$6:$E$10,"Víctor")+SUMIFS('Defensa'!$I$6:$I$10,'Defensa'!$B$6:$B$10,$A37,'Defensa'!$E$6:$E$10,"Ambos")</f>
         <v/>
       </c>
       <c r="E37" s="21">
-        <f>SUMIFS('S1'!$I$6:$I$32,'S1'!$B$6:$B$32,$A37,'S1'!$E$6:$E$32,"Diego")+SUMIFS('S1'!$I$6:$I$32,'S1'!$B$6:$B$32,$A37,'S1'!$E$6:$E$32,"Ambos")+SUMIFS('S2'!$I$6:$I$23,'S2'!$B$6:$B$23,$A37,'S2'!$E$6:$E$23,"Diego")+SUMIFS('S2'!$I$6:$I$23,'S2'!$B$6:$B$23,$A37,'S2'!$E$6:$E$23,"Ambos")+SUMIFS('S3'!$I$6:$I$19,'S3'!$B$6:$B$19,$A37,'S3'!$E$6:$E$19,"Diego")+SUMIFS('S3'!$I$6:$I$19,'S3'!$B$6:$B$19,$A37,'S3'!$E$6:$E$19,"Ambos")+SUMIFS('S4'!$I$6:$I$20,'S4'!$B$6:$B$20,$A37,'S4'!$E$6:$E$20,"Diego")+SUMIFS('S4'!$I$6:$I$20,'S4'!$B$6:$B$20,$A37,'S4'!$E$6:$E$20,"Ambos")+SUMIFS('S5'!$I$6:$I$20,'S5'!$B$6:$B$20,$A37,'S5'!$E$6:$E$20,"Diego")+SUMIFS('S5'!$I$6:$I$20,'S5'!$B$6:$B$20,$A37,'S5'!$E$6:$E$20,"Ambos")+SUMIFS('S6'!$I$6:$I$17,'S6'!$B$6:$B$17,$A37,'S6'!$E$6:$E$17,"Diego")+SUMIFS('S6'!$I$6:$I$17,'S6'!$B$6:$B$17,$A37,'S6'!$E$6:$E$17,"Ambos")+SUMIFS('S7'!$I$6:$I$19,'S7'!$B$6:$B$19,$A37,'S7'!$E$6:$E$19,"Diego")+SUMIFS('S7'!$I$6:$I$19,'S7'!$B$6:$B$19,$A37,'S7'!$E$6:$E$19,"Ambos")+SUMIFS('S8'!$I$6:$I$23,'S8'!$B$6:$B$23,$A37,'S8'!$E$6:$E$23,"Diego")+SUMIFS('S8'!$I$6:$I$23,'S8'!$B$6:$B$23,$A37,'S8'!$E$6:$E$23,"Ambos")+SUMIFS('S9'!$I$6:$I$15,'S9'!$B$6:$B$15,$A37,'S9'!$E$6:$E$15,"Diego")+SUMIFS('S9'!$I$6:$I$15,'S9'!$B$6:$B$15,$A37,'S9'!$E$6:$E$15,"Ambos")+SUMIFS('S10'!$I$6:$I$13,'S10'!$B$6:$B$13,$A37,'S10'!$E$6:$E$13,"Diego")+SUMIFS('S10'!$I$6:$I$13,'S10'!$B$6:$B$13,$A37,'S10'!$E$6:$E$13,"Ambos")+SUMIFS('Holgura'!$I$6:$I$11,'Holgura'!$B$6:$B$11,$A37,'Holgura'!$E$6:$E$11,"Diego")+SUMIFS('Holgura'!$I$6:$I$11,'Holgura'!$B$6:$B$11,$A37,'Holgura'!$E$6:$E$11,"Ambos")+SUMIFS('Entrega'!$I$6:$I$9,'Entrega'!$B$6:$B$9,$A37,'Entrega'!$E$6:$E$9,"Diego")+SUMIFS('Entrega'!$I$6:$I$9,'Entrega'!$B$6:$B$9,$A37,'Entrega'!$E$6:$E$9,"Ambos")+SUMIFS('Defensa'!$I$6:$I$10,'Defensa'!$B$6:$B$10,$A37,'Defensa'!$E$6:$E$10,"Diego")+SUMIFS('Defensa'!$I$6:$I$10,'Defensa'!$B$6:$B$10,$A37,'Defensa'!$E$6:$E$10,"Ambos")</f>
+        <f>SUMIFS('S1'!$I$6:$I$32,'S1'!$B$6:$B$32,$A37,'S1'!$E$6:$E$32,"Diego")+SUMIFS('S1'!$I$6:$I$32,'S1'!$B$6:$B$32,$A37,'S1'!$E$6:$E$32,"Ambos")+SUMIFS('S2'!$I$6:$I$23,'S2'!$B$6:$B$23,$A37,'S2'!$E$6:$E$23,"Diego")+SUMIFS('S2'!$I$6:$I$23,'S2'!$B$6:$B$23,$A37,'S2'!$E$6:$E$23,"Ambos")+SUMIFS('S3'!$I$6:$I$24,'S3'!$B$6:$B$24,$A37,'S3'!$E$6:$E$24,"Diego")+SUMIFS('S3'!$I$6:$I$24,'S3'!$B$6:$B$24,$A37,'S3'!$E$6:$E$24,"Ambos")+SUMIFS('S4'!$I$6:$I$22,'S4'!$B$6:$B$22,$A37,'S4'!$E$6:$E$22,"Diego")+SUMIFS('S4'!$I$6:$I$22,'S4'!$B$6:$B$22,$A37,'S4'!$E$6:$E$22,"Ambos")+SUMIFS('S5'!$I$6:$I$20,'S5'!$B$6:$B$20,$A37,'S5'!$E$6:$E$20,"Diego")+SUMIFS('S5'!$I$6:$I$20,'S5'!$B$6:$B$20,$A37,'S5'!$E$6:$E$20,"Ambos")+SUMIFS('S6'!$I$6:$I$17,'S6'!$B$6:$B$17,$A37,'S6'!$E$6:$E$17,"Diego")+SUMIFS('S6'!$I$6:$I$17,'S6'!$B$6:$B$17,$A37,'S6'!$E$6:$E$17,"Ambos")+SUMIFS('S7'!$I$6:$I$19,'S7'!$B$6:$B$19,$A37,'S7'!$E$6:$E$19,"Diego")+SUMIFS('S7'!$I$6:$I$19,'S7'!$B$6:$B$19,$A37,'S7'!$E$6:$E$19,"Ambos")+SUMIFS('S8'!$I$6:$I$23,'S8'!$B$6:$B$23,$A37,'S8'!$E$6:$E$23,"Diego")+SUMIFS('S8'!$I$6:$I$23,'S8'!$B$6:$B$23,$A37,'S8'!$E$6:$E$23,"Ambos")+SUMIFS('S9'!$I$6:$I$15,'S9'!$B$6:$B$15,$A37,'S9'!$E$6:$E$15,"Diego")+SUMIFS('S9'!$I$6:$I$15,'S9'!$B$6:$B$15,$A37,'S9'!$E$6:$E$15,"Ambos")+SUMIFS('S10'!$I$6:$I$13,'S10'!$B$6:$B$13,$A37,'S10'!$E$6:$E$13,"Diego")+SUMIFS('S10'!$I$6:$I$13,'S10'!$B$6:$B$13,$A37,'S10'!$E$6:$E$13,"Ambos")+SUMIFS('Holgura'!$I$6:$I$11,'Holgura'!$B$6:$B$11,$A37,'Holgura'!$E$6:$E$11,"Diego")+SUMIFS('Holgura'!$I$6:$I$11,'Holgura'!$B$6:$B$11,$A37,'Holgura'!$E$6:$E$11,"Ambos")+SUMIFS('Entrega'!$I$6:$I$9,'Entrega'!$B$6:$B$9,$A37,'Entrega'!$E$6:$E$9,"Diego")+SUMIFS('Entrega'!$I$6:$I$9,'Entrega'!$B$6:$B$9,$A37,'Entrega'!$E$6:$E$9,"Ambos")+SUMIFS('Defensa'!$I$6:$I$10,'Defensa'!$B$6:$B$10,$A37,'Defensa'!$E$6:$E$10,"Diego")+SUMIFS('Defensa'!$I$6:$I$10,'Defensa'!$B$6:$B$10,$A37,'Defensa'!$E$6:$E$10,"Ambos")</f>
         <v/>
       </c>
       <c r="F37" s="21">
-        <f>COUNTIFS('S1'!$B$6:$B$32,$A37,'S1'!$E$6:$E$32,"Víctor")+COUNTIFS('S1'!$B$6:$B$32,$A37,'S1'!$E$6:$E$32,"Ambos")+COUNTIFS('S2'!$B$6:$B$23,$A37,'S2'!$E$6:$E$23,"Víctor")+COUNTIFS('S2'!$B$6:$B$23,$A37,'S2'!$E$6:$E$23,"Ambos")+COUNTIFS('S3'!$B$6:$B$19,$A37,'S3'!$E$6:$E$19,"Víctor")+COUNTIFS('S3'!$B$6:$B$19,$A37,'S3'!$E$6:$E$19,"Ambos")+COUNTIFS('S4'!$B$6:$B$20,$A37,'S4'!$E$6:$E$20,"Víctor")+COUNTIFS('S4'!$B$6:$B$20,$A37,'S4'!$E$6:$E$20,"Ambos")+COUNTIFS('S5'!$B$6:$B$20,$A37,'S5'!$E$6:$E$20,"Víctor")+COUNTIFS('S5'!$B$6:$B$20,$A37,'S5'!$E$6:$E$20,"Ambos")+COUNTIFS('S6'!$B$6:$B$17,$A37,'S6'!$E$6:$E$17,"Víctor")+COUNTIFS('S6'!$B$6:$B$17,$A37,'S6'!$E$6:$E$17,"Ambos")+COUNTIFS('S7'!$B$6:$B$19,$A37,'S7'!$E$6:$E$19,"Víctor")+COUNTIFS('S7'!$B$6:$B$19,$A37,'S7'!$E$6:$E$19,"Ambos")+COUNTIFS('S8'!$B$6:$B$23,$A37,'S8'!$E$6:$E$23,"Víctor")+COUNTIFS('S8'!$B$6:$B$23,$A37,'S8'!$E$6:$E$23,"Ambos")+COUNTIFS('S9'!$B$6:$B$15,$A37,'S9'!$E$6:$E$15,"Víctor")+COUNTIFS('S9'!$B$6:$B$15,$A37,'S9'!$E$6:$E$15,"Ambos")+COUNTIFS('S10'!$B$6:$B$13,$A37,'S10'!$E$6:$E$13,"Víctor")+COUNTIFS('S10'!$B$6:$B$13,$A37,'S10'!$E$6:$E$13,"Ambos")+COUNTIFS('Holgura'!$B$6:$B$11,$A37,'Holgura'!$E$6:$E$11,"Víctor")+COUNTIFS('Holgura'!$B$6:$B$11,$A37,'Holgura'!$E$6:$E$11,"Ambos")+COUNTIFS('Entrega'!$B$6:$B$9,$A37,'Entrega'!$E$6:$E$9,"Víctor")+COUNTIFS('Entrega'!$B$6:$B$9,$A37,'Entrega'!$E$6:$E$9,"Ambos")+COUNTIFS('Defensa'!$B$6:$B$10,$A37,'Defensa'!$E$6:$E$10,"Víctor")+COUNTIFS('Defensa'!$B$6:$B$10,$A37,'Defensa'!$E$6:$E$10,"Ambos")</f>
+        <f>COUNTIFS('S1'!$B$6:$B$32,$A37,'S1'!$E$6:$E$32,"Víctor")+COUNTIFS('S1'!$B$6:$B$32,$A37,'S1'!$E$6:$E$32,"Ambos")+COUNTIFS('S2'!$B$6:$B$23,$A37,'S2'!$E$6:$E$23,"Víctor")+COUNTIFS('S2'!$B$6:$B$23,$A37,'S2'!$E$6:$E$23,"Ambos")+COUNTIFS('S3'!$B$6:$B$24,$A37,'S3'!$E$6:$E$24,"Víctor")+COUNTIFS('S3'!$B$6:$B$24,$A37,'S3'!$E$6:$E$24,"Ambos")+COUNTIFS('S4'!$B$6:$B$22,$A37,'S4'!$E$6:$E$22,"Víctor")+COUNTIFS('S4'!$B$6:$B$22,$A37,'S4'!$E$6:$E$22,"Ambos")+COUNTIFS('S5'!$B$6:$B$20,$A37,'S5'!$E$6:$E$20,"Víctor")+COUNTIFS('S5'!$B$6:$B$20,$A37,'S5'!$E$6:$E$20,"Ambos")+COUNTIFS('S6'!$B$6:$B$17,$A37,'S6'!$E$6:$E$17,"Víctor")+COUNTIFS('S6'!$B$6:$B$17,$A37,'S6'!$E$6:$E$17,"Ambos")+COUNTIFS('S7'!$B$6:$B$19,$A37,'S7'!$E$6:$E$19,"Víctor")+COUNTIFS('S7'!$B$6:$B$19,$A37,'S7'!$E$6:$E$19,"Ambos")+COUNTIFS('S8'!$B$6:$B$23,$A37,'S8'!$E$6:$E$23,"Víctor")+COUNTIFS('S8'!$B$6:$B$23,$A37,'S8'!$E$6:$E$23,"Ambos")+COUNTIFS('S9'!$B$6:$B$15,$A37,'S9'!$E$6:$E$15,"Víctor")+COUNTIFS('S9'!$B$6:$B$15,$A37,'S9'!$E$6:$E$15,"Ambos")+COUNTIFS('S10'!$B$6:$B$13,$A37,'S10'!$E$6:$E$13,"Víctor")+COUNTIFS('S10'!$B$6:$B$13,$A37,'S10'!$E$6:$E$13,"Ambos")+COUNTIFS('Holgura'!$B$6:$B$11,$A37,'Holgura'!$E$6:$E$11,"Víctor")+COUNTIFS('Holgura'!$B$6:$B$11,$A37,'Holgura'!$E$6:$E$11,"Ambos")+COUNTIFS('Entrega'!$B$6:$B$9,$A37,'Entrega'!$E$6:$E$9,"Víctor")+COUNTIFS('Entrega'!$B$6:$B$9,$A37,'Entrega'!$E$6:$E$9,"Ambos")+COUNTIFS('Defensa'!$B$6:$B$10,$A37,'Defensa'!$E$6:$E$10,"Víctor")+COUNTIFS('Defensa'!$B$6:$B$10,$A37,'Defensa'!$E$6:$E$10,"Ambos")</f>
         <v/>
       </c>
       <c r="G37" s="21">
-        <f>COUNTIFS('S1'!$B$6:$B$32,$A37,'S1'!$E$6:$E$32,"Diego")+COUNTIFS('S1'!$B$6:$B$32,$A37,'S1'!$E$6:$E$32,"Ambos")+COUNTIFS('S2'!$B$6:$B$23,$A37,'S2'!$E$6:$E$23,"Diego")+COUNTIFS('S2'!$B$6:$B$23,$A37,'S2'!$E$6:$E$23,"Ambos")+COUNTIFS('S3'!$B$6:$B$19,$A37,'S3'!$E$6:$E$19,"Diego")+COUNTIFS('S3'!$B$6:$B$19,$A37,'S3'!$E$6:$E$19,"Ambos")+COUNTIFS('S4'!$B$6:$B$20,$A37,'S4'!$E$6:$E$20,"Diego")+COUNTIFS('S4'!$B$6:$B$20,$A37,'S4'!$E$6:$E$20,"Ambos")+COUNTIFS('S5'!$B$6:$B$20,$A37,'S5'!$E$6:$E$20,"Diego")+COUNTIFS('S5'!$B$6:$B$20,$A37,'S5'!$E$6:$E$20,"Ambos")+COUNTIFS('S6'!$B$6:$B$17,$A37,'S6'!$E$6:$E$17,"Diego")+COUNTIFS('S6'!$B$6:$B$17,$A37,'S6'!$E$6:$E$17,"Ambos")+COUNTIFS('S7'!$B$6:$B$19,$A37,'S7'!$E$6:$E$19,"Diego")+COUNTIFS('S7'!$B$6:$B$19,$A37,'S7'!$E$6:$E$19,"Ambos")+COUNTIFS('S8'!$B$6:$B$23,$A37,'S8'!$E$6:$E$23,"Diego")+COUNTIFS('S8'!$B$6:$B$23,$A37,'S8'!$E$6:$E$23,"Ambos")+COUNTIFS('S9'!$B$6:$B$15,$A37,'S9'!$E$6:$E$15,"Diego")+COUNTIFS('S9'!$B$6:$B$15,$A37,'S9'!$E$6:$E$15,"Ambos")+COUNTIFS('S10'!$B$6:$B$13,$A37,'S10'!$E$6:$E$13,"Diego")+COUNTIFS('S10'!$B$6:$B$13,$A37,'S10'!$E$6:$E$13,"Ambos")+COUNTIFS('Holgura'!$B$6:$B$11,$A37,'Holgura'!$E$6:$E$11,"Diego")+COUNTIFS('Holgura'!$B$6:$B$11,$A37,'Holgura'!$E$6:$E$11,"Ambos")+COUNTIFS('Entrega'!$B$6:$B$9,$A37,'Entrega'!$E$6:$E$9,"Diego")+COUNTIFS('Entrega'!$B$6:$B$9,$A37,'Entrega'!$E$6:$E$9,"Ambos")+COUNTIFS('Defensa'!$B$6:$B$10,$A37,'Defensa'!$E$6:$E$10,"Diego")+COUNTIFS('Defensa'!$B$6:$B$10,$A37,'Defensa'!$E$6:$E$10,"Ambos")</f>
+        <f>COUNTIFS('S1'!$B$6:$B$32,$A37,'S1'!$E$6:$E$32,"Diego")+COUNTIFS('S1'!$B$6:$B$32,$A37,'S1'!$E$6:$E$32,"Ambos")+COUNTIFS('S2'!$B$6:$B$23,$A37,'S2'!$E$6:$E$23,"Diego")+COUNTIFS('S2'!$B$6:$B$23,$A37,'S2'!$E$6:$E$23,"Ambos")+COUNTIFS('S3'!$B$6:$B$24,$A37,'S3'!$E$6:$E$24,"Diego")+COUNTIFS('S3'!$B$6:$B$24,$A37,'S3'!$E$6:$E$24,"Ambos")+COUNTIFS('S4'!$B$6:$B$22,$A37,'S4'!$E$6:$E$22,"Diego")+COUNTIFS('S4'!$B$6:$B$22,$A37,'S4'!$E$6:$E$22,"Ambos")+COUNTIFS('S5'!$B$6:$B$20,$A37,'S5'!$E$6:$E$20,"Diego")+COUNTIFS('S5'!$B$6:$B$20,$A37,'S5'!$E$6:$E$20,"Ambos")+COUNTIFS('S6'!$B$6:$B$17,$A37,'S6'!$E$6:$E$17,"Diego")+COUNTIFS('S6'!$B$6:$B$17,$A37,'S6'!$E$6:$E$17,"Ambos")+COUNTIFS('S7'!$B$6:$B$19,$A37,'S7'!$E$6:$E$19,"Diego")+COUNTIFS('S7'!$B$6:$B$19,$A37,'S7'!$E$6:$E$19,"Ambos")+COUNTIFS('S8'!$B$6:$B$23,$A37,'S8'!$E$6:$E$23,"Diego")+COUNTIFS('S8'!$B$6:$B$23,$A37,'S8'!$E$6:$E$23,"Ambos")+COUNTIFS('S9'!$B$6:$B$15,$A37,'S9'!$E$6:$E$15,"Diego")+COUNTIFS('S9'!$B$6:$B$15,$A37,'S9'!$E$6:$E$15,"Ambos")+COUNTIFS('S10'!$B$6:$B$13,$A37,'S10'!$E$6:$E$13,"Diego")+COUNTIFS('S10'!$B$6:$B$13,$A37,'S10'!$E$6:$E$13,"Ambos")+COUNTIFS('Holgura'!$B$6:$B$11,$A37,'Holgura'!$E$6:$E$11,"Diego")+COUNTIFS('Holgura'!$B$6:$B$11,$A37,'Holgura'!$E$6:$E$11,"Ambos")+COUNTIFS('Entrega'!$B$6:$B$9,$A37,'Entrega'!$E$6:$E$9,"Diego")+COUNTIFS('Entrega'!$B$6:$B$9,$A37,'Entrega'!$E$6:$E$9,"Ambos")+COUNTIFS('Defensa'!$B$6:$B$10,$A37,'Defensa'!$E$6:$E$10,"Diego")+COUNTIFS('Defensa'!$B$6:$B$10,$A37,'Defensa'!$E$6:$E$10,"Ambos")</f>
         <v/>
       </c>
     </row>
@@ -9637,19 +9658,19 @@
         <v/>
       </c>
       <c r="D38" s="21">
-        <f>SUMIFS('S1'!$I$6:$I$32,'S1'!$B$6:$B$32,$A38,'S1'!$E$6:$E$32,"Víctor")+SUMIFS('S1'!$I$6:$I$32,'S1'!$B$6:$B$32,$A38,'S1'!$E$6:$E$32,"Ambos")+SUMIFS('S2'!$I$6:$I$23,'S2'!$B$6:$B$23,$A38,'S2'!$E$6:$E$23,"Víctor")+SUMIFS('S2'!$I$6:$I$23,'S2'!$B$6:$B$23,$A38,'S2'!$E$6:$E$23,"Ambos")+SUMIFS('S3'!$I$6:$I$19,'S3'!$B$6:$B$19,$A38,'S3'!$E$6:$E$19,"Víctor")+SUMIFS('S3'!$I$6:$I$19,'S3'!$B$6:$B$19,$A38,'S3'!$E$6:$E$19,"Ambos")+SUMIFS('S4'!$I$6:$I$20,'S4'!$B$6:$B$20,$A38,'S4'!$E$6:$E$20,"Víctor")+SUMIFS('S4'!$I$6:$I$20,'S4'!$B$6:$B$20,$A38,'S4'!$E$6:$E$20,"Ambos")+SUMIFS('S5'!$I$6:$I$20,'S5'!$B$6:$B$20,$A38,'S5'!$E$6:$E$20,"Víctor")+SUMIFS('S5'!$I$6:$I$20,'S5'!$B$6:$B$20,$A38,'S5'!$E$6:$E$20,"Ambos")+SUMIFS('S6'!$I$6:$I$17,'S6'!$B$6:$B$17,$A38,'S6'!$E$6:$E$17,"Víctor")+SUMIFS('S6'!$I$6:$I$17,'S6'!$B$6:$B$17,$A38,'S6'!$E$6:$E$17,"Ambos")+SUMIFS('S7'!$I$6:$I$19,'S7'!$B$6:$B$19,$A38,'S7'!$E$6:$E$19,"Víctor")+SUMIFS('S7'!$I$6:$I$19,'S7'!$B$6:$B$19,$A38,'S7'!$E$6:$E$19,"Ambos")+SUMIFS('S8'!$I$6:$I$23,'S8'!$B$6:$B$23,$A38,'S8'!$E$6:$E$23,"Víctor")+SUMIFS('S8'!$I$6:$I$23,'S8'!$B$6:$B$23,$A38,'S8'!$E$6:$E$23,"Ambos")+SUMIFS('S9'!$I$6:$I$15,'S9'!$B$6:$B$15,$A38,'S9'!$E$6:$E$15,"Víctor")+SUMIFS('S9'!$I$6:$I$15,'S9'!$B$6:$B$15,$A38,'S9'!$E$6:$E$15,"Ambos")+SUMIFS('S10'!$I$6:$I$13,'S10'!$B$6:$B$13,$A38,'S10'!$E$6:$E$13,"Víctor")+SUMIFS('S10'!$I$6:$I$13,'S10'!$B$6:$B$13,$A38,'S10'!$E$6:$E$13,"Ambos")+SUMIFS('Holgura'!$I$6:$I$11,'Holgura'!$B$6:$B$11,$A38,'Holgura'!$E$6:$E$11,"Víctor")+SUMIFS('Holgura'!$I$6:$I$11,'Holgura'!$B$6:$B$11,$A38,'Holgura'!$E$6:$E$11,"Ambos")+SUMIFS('Entrega'!$I$6:$I$9,'Entrega'!$B$6:$B$9,$A38,'Entrega'!$E$6:$E$9,"Víctor")+SUMIFS('Entrega'!$I$6:$I$9,'Entrega'!$B$6:$B$9,$A38,'Entrega'!$E$6:$E$9,"Ambos")+SUMIFS('Defensa'!$I$6:$I$10,'Defensa'!$B$6:$B$10,$A38,'Defensa'!$E$6:$E$10,"Víctor")+SUMIFS('Defensa'!$I$6:$I$10,'Defensa'!$B$6:$B$10,$A38,'Defensa'!$E$6:$E$10,"Ambos")</f>
+        <f>SUMIFS('S1'!$I$6:$I$32,'S1'!$B$6:$B$32,$A38,'S1'!$E$6:$E$32,"Víctor")+SUMIFS('S1'!$I$6:$I$32,'S1'!$B$6:$B$32,$A38,'S1'!$E$6:$E$32,"Ambos")+SUMIFS('S2'!$I$6:$I$23,'S2'!$B$6:$B$23,$A38,'S2'!$E$6:$E$23,"Víctor")+SUMIFS('S2'!$I$6:$I$23,'S2'!$B$6:$B$23,$A38,'S2'!$E$6:$E$23,"Ambos")+SUMIFS('S3'!$I$6:$I$24,'S3'!$B$6:$B$24,$A38,'S3'!$E$6:$E$24,"Víctor")+SUMIFS('S3'!$I$6:$I$24,'S3'!$B$6:$B$24,$A38,'S3'!$E$6:$E$24,"Ambos")+SUMIFS('S4'!$I$6:$I$22,'S4'!$B$6:$B$22,$A38,'S4'!$E$6:$E$22,"Víctor")+SUMIFS('S4'!$I$6:$I$22,'S4'!$B$6:$B$22,$A38,'S4'!$E$6:$E$22,"Ambos")+SUMIFS('S5'!$I$6:$I$20,'S5'!$B$6:$B$20,$A38,'S5'!$E$6:$E$20,"Víctor")+SUMIFS('S5'!$I$6:$I$20,'S5'!$B$6:$B$20,$A38,'S5'!$E$6:$E$20,"Ambos")+SUMIFS('S6'!$I$6:$I$17,'S6'!$B$6:$B$17,$A38,'S6'!$E$6:$E$17,"Víctor")+SUMIFS('S6'!$I$6:$I$17,'S6'!$B$6:$B$17,$A38,'S6'!$E$6:$E$17,"Ambos")+SUMIFS('S7'!$I$6:$I$19,'S7'!$B$6:$B$19,$A38,'S7'!$E$6:$E$19,"Víctor")+SUMIFS('S7'!$I$6:$I$19,'S7'!$B$6:$B$19,$A38,'S7'!$E$6:$E$19,"Ambos")+SUMIFS('S8'!$I$6:$I$23,'S8'!$B$6:$B$23,$A38,'S8'!$E$6:$E$23,"Víctor")+SUMIFS('S8'!$I$6:$I$23,'S8'!$B$6:$B$23,$A38,'S8'!$E$6:$E$23,"Ambos")+SUMIFS('S9'!$I$6:$I$15,'S9'!$B$6:$B$15,$A38,'S9'!$E$6:$E$15,"Víctor")+SUMIFS('S9'!$I$6:$I$15,'S9'!$B$6:$B$15,$A38,'S9'!$E$6:$E$15,"Ambos")+SUMIFS('S10'!$I$6:$I$13,'S10'!$B$6:$B$13,$A38,'S10'!$E$6:$E$13,"Víctor")+SUMIFS('S10'!$I$6:$I$13,'S10'!$B$6:$B$13,$A38,'S10'!$E$6:$E$13,"Ambos")+SUMIFS('Holgura'!$I$6:$I$11,'Holgura'!$B$6:$B$11,$A38,'Holgura'!$E$6:$E$11,"Víctor")+SUMIFS('Holgura'!$I$6:$I$11,'Holgura'!$B$6:$B$11,$A38,'Holgura'!$E$6:$E$11,"Ambos")+SUMIFS('Entrega'!$I$6:$I$9,'Entrega'!$B$6:$B$9,$A38,'Entrega'!$E$6:$E$9,"Víctor")+SUMIFS('Entrega'!$I$6:$I$9,'Entrega'!$B$6:$B$9,$A38,'Entrega'!$E$6:$E$9,"Ambos")+SUMIFS('Defensa'!$I$6:$I$10,'Defensa'!$B$6:$B$10,$A38,'Defensa'!$E$6:$E$10,"Víctor")+SUMIFS('Defensa'!$I$6:$I$10,'Defensa'!$B$6:$B$10,$A38,'Defensa'!$E$6:$E$10,"Ambos")</f>
         <v/>
       </c>
       <c r="E38" s="21">
-        <f>SUMIFS('S1'!$I$6:$I$32,'S1'!$B$6:$B$32,$A38,'S1'!$E$6:$E$32,"Diego")+SUMIFS('S1'!$I$6:$I$32,'S1'!$B$6:$B$32,$A38,'S1'!$E$6:$E$32,"Ambos")+SUMIFS('S2'!$I$6:$I$23,'S2'!$B$6:$B$23,$A38,'S2'!$E$6:$E$23,"Diego")+SUMIFS('S2'!$I$6:$I$23,'S2'!$B$6:$B$23,$A38,'S2'!$E$6:$E$23,"Ambos")+SUMIFS('S3'!$I$6:$I$19,'S3'!$B$6:$B$19,$A38,'S3'!$E$6:$E$19,"Diego")+SUMIFS('S3'!$I$6:$I$19,'S3'!$B$6:$B$19,$A38,'S3'!$E$6:$E$19,"Ambos")+SUMIFS('S4'!$I$6:$I$20,'S4'!$B$6:$B$20,$A38,'S4'!$E$6:$E$20,"Diego")+SUMIFS('S4'!$I$6:$I$20,'S4'!$B$6:$B$20,$A38,'S4'!$E$6:$E$20,"Ambos")+SUMIFS('S5'!$I$6:$I$20,'S5'!$B$6:$B$20,$A38,'S5'!$E$6:$E$20,"Diego")+SUMIFS('S5'!$I$6:$I$20,'S5'!$B$6:$B$20,$A38,'S5'!$E$6:$E$20,"Ambos")+SUMIFS('S6'!$I$6:$I$17,'S6'!$B$6:$B$17,$A38,'S6'!$E$6:$E$17,"Diego")+SUMIFS('S6'!$I$6:$I$17,'S6'!$B$6:$B$17,$A38,'S6'!$E$6:$E$17,"Ambos")+SUMIFS('S7'!$I$6:$I$19,'S7'!$B$6:$B$19,$A38,'S7'!$E$6:$E$19,"Diego")+SUMIFS('S7'!$I$6:$I$19,'S7'!$B$6:$B$19,$A38,'S7'!$E$6:$E$19,"Ambos")+SUMIFS('S8'!$I$6:$I$23,'S8'!$B$6:$B$23,$A38,'S8'!$E$6:$E$23,"Diego")+SUMIFS('S8'!$I$6:$I$23,'S8'!$B$6:$B$23,$A38,'S8'!$E$6:$E$23,"Ambos")+SUMIFS('S9'!$I$6:$I$15,'S9'!$B$6:$B$15,$A38,'S9'!$E$6:$E$15,"Diego")+SUMIFS('S9'!$I$6:$I$15,'S9'!$B$6:$B$15,$A38,'S9'!$E$6:$E$15,"Ambos")+SUMIFS('S10'!$I$6:$I$13,'S10'!$B$6:$B$13,$A38,'S10'!$E$6:$E$13,"Diego")+SUMIFS('S10'!$I$6:$I$13,'S10'!$B$6:$B$13,$A38,'S10'!$E$6:$E$13,"Ambos")+SUMIFS('Holgura'!$I$6:$I$11,'Holgura'!$B$6:$B$11,$A38,'Holgura'!$E$6:$E$11,"Diego")+SUMIFS('Holgura'!$I$6:$I$11,'Holgura'!$B$6:$B$11,$A38,'Holgura'!$E$6:$E$11,"Ambos")+SUMIFS('Entrega'!$I$6:$I$9,'Entrega'!$B$6:$B$9,$A38,'Entrega'!$E$6:$E$9,"Diego")+SUMIFS('Entrega'!$I$6:$I$9,'Entrega'!$B$6:$B$9,$A38,'Entrega'!$E$6:$E$9,"Ambos")+SUMIFS('Defensa'!$I$6:$I$10,'Defensa'!$B$6:$B$10,$A38,'Defensa'!$E$6:$E$10,"Diego")+SUMIFS('Defensa'!$I$6:$I$10,'Defensa'!$B$6:$B$10,$A38,'Defensa'!$E$6:$E$10,"Ambos")</f>
+        <f>SUMIFS('S1'!$I$6:$I$32,'S1'!$B$6:$B$32,$A38,'S1'!$E$6:$E$32,"Diego")+SUMIFS('S1'!$I$6:$I$32,'S1'!$B$6:$B$32,$A38,'S1'!$E$6:$E$32,"Ambos")+SUMIFS('S2'!$I$6:$I$23,'S2'!$B$6:$B$23,$A38,'S2'!$E$6:$E$23,"Diego")+SUMIFS('S2'!$I$6:$I$23,'S2'!$B$6:$B$23,$A38,'S2'!$E$6:$E$23,"Ambos")+SUMIFS('S3'!$I$6:$I$24,'S3'!$B$6:$B$24,$A38,'S3'!$E$6:$E$24,"Diego")+SUMIFS('S3'!$I$6:$I$24,'S3'!$B$6:$B$24,$A38,'S3'!$E$6:$E$24,"Ambos")+SUMIFS('S4'!$I$6:$I$22,'S4'!$B$6:$B$22,$A38,'S4'!$E$6:$E$22,"Diego")+SUMIFS('S4'!$I$6:$I$22,'S4'!$B$6:$B$22,$A38,'S4'!$E$6:$E$22,"Ambos")+SUMIFS('S5'!$I$6:$I$20,'S5'!$B$6:$B$20,$A38,'S5'!$E$6:$E$20,"Diego")+SUMIFS('S5'!$I$6:$I$20,'S5'!$B$6:$B$20,$A38,'S5'!$E$6:$E$20,"Ambos")+SUMIFS('S6'!$I$6:$I$17,'S6'!$B$6:$B$17,$A38,'S6'!$E$6:$E$17,"Diego")+SUMIFS('S6'!$I$6:$I$17,'S6'!$B$6:$B$17,$A38,'S6'!$E$6:$E$17,"Ambos")+SUMIFS('S7'!$I$6:$I$19,'S7'!$B$6:$B$19,$A38,'S7'!$E$6:$E$19,"Diego")+SUMIFS('S7'!$I$6:$I$19,'S7'!$B$6:$B$19,$A38,'S7'!$E$6:$E$19,"Ambos")+SUMIFS('S8'!$I$6:$I$23,'S8'!$B$6:$B$23,$A38,'S8'!$E$6:$E$23,"Diego")+SUMIFS('S8'!$I$6:$I$23,'S8'!$B$6:$B$23,$A38,'S8'!$E$6:$E$23,"Ambos")+SUMIFS('S9'!$I$6:$I$15,'S9'!$B$6:$B$15,$A38,'S9'!$E$6:$E$15,"Diego")+SUMIFS('S9'!$I$6:$I$15,'S9'!$B$6:$B$15,$A38,'S9'!$E$6:$E$15,"Ambos")+SUMIFS('S10'!$I$6:$I$13,'S10'!$B$6:$B$13,$A38,'S10'!$E$6:$E$13,"Diego")+SUMIFS('S10'!$I$6:$I$13,'S10'!$B$6:$B$13,$A38,'S10'!$E$6:$E$13,"Ambos")+SUMIFS('Holgura'!$I$6:$I$11,'Holgura'!$B$6:$B$11,$A38,'Holgura'!$E$6:$E$11,"Diego")+SUMIFS('Holgura'!$I$6:$I$11,'Holgura'!$B$6:$B$11,$A38,'Holgura'!$E$6:$E$11,"Ambos")+SUMIFS('Entrega'!$I$6:$I$9,'Entrega'!$B$6:$B$9,$A38,'Entrega'!$E$6:$E$9,"Diego")+SUMIFS('Entrega'!$I$6:$I$9,'Entrega'!$B$6:$B$9,$A38,'Entrega'!$E$6:$E$9,"Ambos")+SUMIFS('Defensa'!$I$6:$I$10,'Defensa'!$B$6:$B$10,$A38,'Defensa'!$E$6:$E$10,"Diego")+SUMIFS('Defensa'!$I$6:$I$10,'Defensa'!$B$6:$B$10,$A38,'Defensa'!$E$6:$E$10,"Ambos")</f>
         <v/>
       </c>
       <c r="F38" s="21">
-        <f>COUNTIFS('S1'!$B$6:$B$32,$A38,'S1'!$E$6:$E$32,"Víctor")+COUNTIFS('S1'!$B$6:$B$32,$A38,'S1'!$E$6:$E$32,"Ambos")+COUNTIFS('S2'!$B$6:$B$23,$A38,'S2'!$E$6:$E$23,"Víctor")+COUNTIFS('S2'!$B$6:$B$23,$A38,'S2'!$E$6:$E$23,"Ambos")+COUNTIFS('S3'!$B$6:$B$19,$A38,'S3'!$E$6:$E$19,"Víctor")+COUNTIFS('S3'!$B$6:$B$19,$A38,'S3'!$E$6:$E$19,"Ambos")+COUNTIFS('S4'!$B$6:$B$20,$A38,'S4'!$E$6:$E$20,"Víctor")+COUNTIFS('S4'!$B$6:$B$20,$A38,'S4'!$E$6:$E$20,"Ambos")+COUNTIFS('S5'!$B$6:$B$20,$A38,'S5'!$E$6:$E$20,"Víctor")+COUNTIFS('S5'!$B$6:$B$20,$A38,'S5'!$E$6:$E$20,"Ambos")+COUNTIFS('S6'!$B$6:$B$17,$A38,'S6'!$E$6:$E$17,"Víctor")+COUNTIFS('S6'!$B$6:$B$17,$A38,'S6'!$E$6:$E$17,"Ambos")+COUNTIFS('S7'!$B$6:$B$19,$A38,'S7'!$E$6:$E$19,"Víctor")+COUNTIFS('S7'!$B$6:$B$19,$A38,'S7'!$E$6:$E$19,"Ambos")+COUNTIFS('S8'!$B$6:$B$23,$A38,'S8'!$E$6:$E$23,"Víctor")+COUNTIFS('S8'!$B$6:$B$23,$A38,'S8'!$E$6:$E$23,"Ambos")+COUNTIFS('S9'!$B$6:$B$15,$A38,'S9'!$E$6:$E$15,"Víctor")+COUNTIFS('S9'!$B$6:$B$15,$A38,'S9'!$E$6:$E$15,"Ambos")+COUNTIFS('S10'!$B$6:$B$13,$A38,'S10'!$E$6:$E$13,"Víctor")+COUNTIFS('S10'!$B$6:$B$13,$A38,'S10'!$E$6:$E$13,"Ambos")+COUNTIFS('Holgura'!$B$6:$B$11,$A38,'Holgura'!$E$6:$E$11,"Víctor")+COUNTIFS('Holgura'!$B$6:$B$11,$A38,'Holgura'!$E$6:$E$11,"Ambos")+COUNTIFS('Entrega'!$B$6:$B$9,$A38,'Entrega'!$E$6:$E$9,"Víctor")+COUNTIFS('Entrega'!$B$6:$B$9,$A38,'Entrega'!$E$6:$E$9,"Ambos")+COUNTIFS('Defensa'!$B$6:$B$10,$A38,'Defensa'!$E$6:$E$10,"Víctor")+COUNTIFS('Defensa'!$B$6:$B$10,$A38,'Defensa'!$E$6:$E$10,"Ambos")</f>
+        <f>COUNTIFS('S1'!$B$6:$B$32,$A38,'S1'!$E$6:$E$32,"Víctor")+COUNTIFS('S1'!$B$6:$B$32,$A38,'S1'!$E$6:$E$32,"Ambos")+COUNTIFS('S2'!$B$6:$B$23,$A38,'S2'!$E$6:$E$23,"Víctor")+COUNTIFS('S2'!$B$6:$B$23,$A38,'S2'!$E$6:$E$23,"Ambos")+COUNTIFS('S3'!$B$6:$B$24,$A38,'S3'!$E$6:$E$24,"Víctor")+COUNTIFS('S3'!$B$6:$B$24,$A38,'S3'!$E$6:$E$24,"Ambos")+COUNTIFS('S4'!$B$6:$B$22,$A38,'S4'!$E$6:$E$22,"Víctor")+COUNTIFS('S4'!$B$6:$B$22,$A38,'S4'!$E$6:$E$22,"Ambos")+COUNTIFS('S5'!$B$6:$B$20,$A38,'S5'!$E$6:$E$20,"Víctor")+COUNTIFS('S5'!$B$6:$B$20,$A38,'S5'!$E$6:$E$20,"Ambos")+COUNTIFS('S6'!$B$6:$B$17,$A38,'S6'!$E$6:$E$17,"Víctor")+COUNTIFS('S6'!$B$6:$B$17,$A38,'S6'!$E$6:$E$17,"Ambos")+COUNTIFS('S7'!$B$6:$B$19,$A38,'S7'!$E$6:$E$19,"Víctor")+COUNTIFS('S7'!$B$6:$B$19,$A38,'S7'!$E$6:$E$19,"Ambos")+COUNTIFS('S8'!$B$6:$B$23,$A38,'S8'!$E$6:$E$23,"Víctor")+COUNTIFS('S8'!$B$6:$B$23,$A38,'S8'!$E$6:$E$23,"Ambos")+COUNTIFS('S9'!$B$6:$B$15,$A38,'S9'!$E$6:$E$15,"Víctor")+COUNTIFS('S9'!$B$6:$B$15,$A38,'S9'!$E$6:$E$15,"Ambos")+COUNTIFS('S10'!$B$6:$B$13,$A38,'S10'!$E$6:$E$13,"Víctor")+COUNTIFS('S10'!$B$6:$B$13,$A38,'S10'!$E$6:$E$13,"Ambos")+COUNTIFS('Holgura'!$B$6:$B$11,$A38,'Holgura'!$E$6:$E$11,"Víctor")+COUNTIFS('Holgura'!$B$6:$B$11,$A38,'Holgura'!$E$6:$E$11,"Ambos")+COUNTIFS('Entrega'!$B$6:$B$9,$A38,'Entrega'!$E$6:$E$9,"Víctor")+COUNTIFS('Entrega'!$B$6:$B$9,$A38,'Entrega'!$E$6:$E$9,"Ambos")+COUNTIFS('Defensa'!$B$6:$B$10,$A38,'Defensa'!$E$6:$E$10,"Víctor")+COUNTIFS('Defensa'!$B$6:$B$10,$A38,'Defensa'!$E$6:$E$10,"Ambos")</f>
         <v/>
       </c>
       <c r="G38" s="21">
-        <f>COUNTIFS('S1'!$B$6:$B$32,$A38,'S1'!$E$6:$E$32,"Diego")+COUNTIFS('S1'!$B$6:$B$32,$A38,'S1'!$E$6:$E$32,"Ambos")+COUNTIFS('S2'!$B$6:$B$23,$A38,'S2'!$E$6:$E$23,"Diego")+COUNTIFS('S2'!$B$6:$B$23,$A38,'S2'!$E$6:$E$23,"Ambos")+COUNTIFS('S3'!$B$6:$B$19,$A38,'S3'!$E$6:$E$19,"Diego")+COUNTIFS('S3'!$B$6:$B$19,$A38,'S3'!$E$6:$E$19,"Ambos")+COUNTIFS('S4'!$B$6:$B$20,$A38,'S4'!$E$6:$E$20,"Diego")+COUNTIFS('S4'!$B$6:$B$20,$A38,'S4'!$E$6:$E$20,"Ambos")+COUNTIFS('S5'!$B$6:$B$20,$A38,'S5'!$E$6:$E$20,"Diego")+COUNTIFS('S5'!$B$6:$B$20,$A38,'S5'!$E$6:$E$20,"Ambos")+COUNTIFS('S6'!$B$6:$B$17,$A38,'S6'!$E$6:$E$17,"Diego")+COUNTIFS('S6'!$B$6:$B$17,$A38,'S6'!$E$6:$E$17,"Ambos")+COUNTIFS('S7'!$B$6:$B$19,$A38,'S7'!$E$6:$E$19,"Diego")+COUNTIFS('S7'!$B$6:$B$19,$A38,'S7'!$E$6:$E$19,"Ambos")+COUNTIFS('S8'!$B$6:$B$23,$A38,'S8'!$E$6:$E$23,"Diego")+COUNTIFS('S8'!$B$6:$B$23,$A38,'S8'!$E$6:$E$23,"Ambos")+COUNTIFS('S9'!$B$6:$B$15,$A38,'S9'!$E$6:$E$15,"Diego")+COUNTIFS('S9'!$B$6:$B$15,$A38,'S9'!$E$6:$E$15,"Ambos")+COUNTIFS('S10'!$B$6:$B$13,$A38,'S10'!$E$6:$E$13,"Diego")+COUNTIFS('S10'!$B$6:$B$13,$A38,'S10'!$E$6:$E$13,"Ambos")+COUNTIFS('Holgura'!$B$6:$B$11,$A38,'Holgura'!$E$6:$E$11,"Diego")+COUNTIFS('Holgura'!$B$6:$B$11,$A38,'Holgura'!$E$6:$E$11,"Ambos")+COUNTIFS('Entrega'!$B$6:$B$9,$A38,'Entrega'!$E$6:$E$9,"Diego")+COUNTIFS('Entrega'!$B$6:$B$9,$A38,'Entrega'!$E$6:$E$9,"Ambos")+COUNTIFS('Defensa'!$B$6:$B$10,$A38,'Defensa'!$E$6:$E$10,"Diego")+COUNTIFS('Defensa'!$B$6:$B$10,$A38,'Defensa'!$E$6:$E$10,"Ambos")</f>
+        <f>COUNTIFS('S1'!$B$6:$B$32,$A38,'S1'!$E$6:$E$32,"Diego")+COUNTIFS('S1'!$B$6:$B$32,$A38,'S1'!$E$6:$E$32,"Ambos")+COUNTIFS('S2'!$B$6:$B$23,$A38,'S2'!$E$6:$E$23,"Diego")+COUNTIFS('S2'!$B$6:$B$23,$A38,'S2'!$E$6:$E$23,"Ambos")+COUNTIFS('S3'!$B$6:$B$24,$A38,'S3'!$E$6:$E$24,"Diego")+COUNTIFS('S3'!$B$6:$B$24,$A38,'S3'!$E$6:$E$24,"Ambos")+COUNTIFS('S4'!$B$6:$B$22,$A38,'S4'!$E$6:$E$22,"Diego")+COUNTIFS('S4'!$B$6:$B$22,$A38,'S4'!$E$6:$E$22,"Ambos")+COUNTIFS('S5'!$B$6:$B$20,$A38,'S5'!$E$6:$E$20,"Diego")+COUNTIFS('S5'!$B$6:$B$20,$A38,'S5'!$E$6:$E$20,"Ambos")+COUNTIFS('S6'!$B$6:$B$17,$A38,'S6'!$E$6:$E$17,"Diego")+COUNTIFS('S6'!$B$6:$B$17,$A38,'S6'!$E$6:$E$17,"Ambos")+COUNTIFS('S7'!$B$6:$B$19,$A38,'S7'!$E$6:$E$19,"Diego")+COUNTIFS('S7'!$B$6:$B$19,$A38,'S7'!$E$6:$E$19,"Ambos")+COUNTIFS('S8'!$B$6:$B$23,$A38,'S8'!$E$6:$E$23,"Diego")+COUNTIFS('S8'!$B$6:$B$23,$A38,'S8'!$E$6:$E$23,"Ambos")+COUNTIFS('S9'!$B$6:$B$15,$A38,'S9'!$E$6:$E$15,"Diego")+COUNTIFS('S9'!$B$6:$B$15,$A38,'S9'!$E$6:$E$15,"Ambos")+COUNTIFS('S10'!$B$6:$B$13,$A38,'S10'!$E$6:$E$13,"Diego")+COUNTIFS('S10'!$B$6:$B$13,$A38,'S10'!$E$6:$E$13,"Ambos")+COUNTIFS('Holgura'!$B$6:$B$11,$A38,'Holgura'!$E$6:$E$11,"Diego")+COUNTIFS('Holgura'!$B$6:$B$11,$A38,'Holgura'!$E$6:$E$11,"Ambos")+COUNTIFS('Entrega'!$B$6:$B$9,$A38,'Entrega'!$E$6:$E$9,"Diego")+COUNTIFS('Entrega'!$B$6:$B$9,$A38,'Entrega'!$E$6:$E$9,"Ambos")+COUNTIFS('Defensa'!$B$6:$B$10,$A38,'Defensa'!$E$6:$E$10,"Diego")+COUNTIFS('Defensa'!$B$6:$B$10,$A38,'Defensa'!$E$6:$E$10,"Ambos")</f>
         <v/>
       </c>
     </row>
@@ -9666,19 +9687,19 @@
         <v/>
       </c>
       <c r="D39" s="21">
-        <f>SUMIFS('S1'!$I$6:$I$32,'S1'!$B$6:$B$32,$A39,'S1'!$E$6:$E$32,"Víctor")+SUMIFS('S1'!$I$6:$I$32,'S1'!$B$6:$B$32,$A39,'S1'!$E$6:$E$32,"Ambos")+SUMIFS('S2'!$I$6:$I$23,'S2'!$B$6:$B$23,$A39,'S2'!$E$6:$E$23,"Víctor")+SUMIFS('S2'!$I$6:$I$23,'S2'!$B$6:$B$23,$A39,'S2'!$E$6:$E$23,"Ambos")+SUMIFS('S3'!$I$6:$I$19,'S3'!$B$6:$B$19,$A39,'S3'!$E$6:$E$19,"Víctor")+SUMIFS('S3'!$I$6:$I$19,'S3'!$B$6:$B$19,$A39,'S3'!$E$6:$E$19,"Ambos")+SUMIFS('S4'!$I$6:$I$20,'S4'!$B$6:$B$20,$A39,'S4'!$E$6:$E$20,"Víctor")+SUMIFS('S4'!$I$6:$I$20,'S4'!$B$6:$B$20,$A39,'S4'!$E$6:$E$20,"Ambos")+SUMIFS('S5'!$I$6:$I$20,'S5'!$B$6:$B$20,$A39,'S5'!$E$6:$E$20,"Víctor")+SUMIFS('S5'!$I$6:$I$20,'S5'!$B$6:$B$20,$A39,'S5'!$E$6:$E$20,"Ambos")+SUMIFS('S6'!$I$6:$I$17,'S6'!$B$6:$B$17,$A39,'S6'!$E$6:$E$17,"Víctor")+SUMIFS('S6'!$I$6:$I$17,'S6'!$B$6:$B$17,$A39,'S6'!$E$6:$E$17,"Ambos")+SUMIFS('S7'!$I$6:$I$19,'S7'!$B$6:$B$19,$A39,'S7'!$E$6:$E$19,"Víctor")+SUMIFS('S7'!$I$6:$I$19,'S7'!$B$6:$B$19,$A39,'S7'!$E$6:$E$19,"Ambos")+SUMIFS('S8'!$I$6:$I$23,'S8'!$B$6:$B$23,$A39,'S8'!$E$6:$E$23,"Víctor")+SUMIFS('S8'!$I$6:$I$23,'S8'!$B$6:$B$23,$A39,'S8'!$E$6:$E$23,"Ambos")+SUMIFS('S9'!$I$6:$I$15,'S9'!$B$6:$B$15,$A39,'S9'!$E$6:$E$15,"Víctor")+SUMIFS('S9'!$I$6:$I$15,'S9'!$B$6:$B$15,$A39,'S9'!$E$6:$E$15,"Ambos")+SUMIFS('S10'!$I$6:$I$13,'S10'!$B$6:$B$13,$A39,'S10'!$E$6:$E$13,"Víctor")+SUMIFS('S10'!$I$6:$I$13,'S10'!$B$6:$B$13,$A39,'S10'!$E$6:$E$13,"Ambos")+SUMIFS('Holgura'!$I$6:$I$11,'Holgura'!$B$6:$B$11,$A39,'Holgura'!$E$6:$E$11,"Víctor")+SUMIFS('Holgura'!$I$6:$I$11,'Holgura'!$B$6:$B$11,$A39,'Holgura'!$E$6:$E$11,"Ambos")+SUMIFS('Entrega'!$I$6:$I$9,'Entrega'!$B$6:$B$9,$A39,'Entrega'!$E$6:$E$9,"Víctor")+SUMIFS('Entrega'!$I$6:$I$9,'Entrega'!$B$6:$B$9,$A39,'Entrega'!$E$6:$E$9,"Ambos")+SUMIFS('Defensa'!$I$6:$I$10,'Defensa'!$B$6:$B$10,$A39,'Defensa'!$E$6:$E$10,"Víctor")+SUMIFS('Defensa'!$I$6:$I$10,'Defensa'!$B$6:$B$10,$A39,'Defensa'!$E$6:$E$10,"Ambos")</f>
+        <f>SUMIFS('S1'!$I$6:$I$32,'S1'!$B$6:$B$32,$A39,'S1'!$E$6:$E$32,"Víctor")+SUMIFS('S1'!$I$6:$I$32,'S1'!$B$6:$B$32,$A39,'S1'!$E$6:$E$32,"Ambos")+SUMIFS('S2'!$I$6:$I$23,'S2'!$B$6:$B$23,$A39,'S2'!$E$6:$E$23,"Víctor")+SUMIFS('S2'!$I$6:$I$23,'S2'!$B$6:$B$23,$A39,'S2'!$E$6:$E$23,"Ambos")+SUMIFS('S3'!$I$6:$I$24,'S3'!$B$6:$B$24,$A39,'S3'!$E$6:$E$24,"Víctor")+SUMIFS('S3'!$I$6:$I$24,'S3'!$B$6:$B$24,$A39,'S3'!$E$6:$E$24,"Ambos")+SUMIFS('S4'!$I$6:$I$22,'S4'!$B$6:$B$22,$A39,'S4'!$E$6:$E$22,"Víctor")+SUMIFS('S4'!$I$6:$I$22,'S4'!$B$6:$B$22,$A39,'S4'!$E$6:$E$22,"Ambos")+SUMIFS('S5'!$I$6:$I$20,'S5'!$B$6:$B$20,$A39,'S5'!$E$6:$E$20,"Víctor")+SUMIFS('S5'!$I$6:$I$20,'S5'!$B$6:$B$20,$A39,'S5'!$E$6:$E$20,"Ambos")+SUMIFS('S6'!$I$6:$I$17,'S6'!$B$6:$B$17,$A39,'S6'!$E$6:$E$17,"Víctor")+SUMIFS('S6'!$I$6:$I$17,'S6'!$B$6:$B$17,$A39,'S6'!$E$6:$E$17,"Ambos")+SUMIFS('S7'!$I$6:$I$19,'S7'!$B$6:$B$19,$A39,'S7'!$E$6:$E$19,"Víctor")+SUMIFS('S7'!$I$6:$I$19,'S7'!$B$6:$B$19,$A39,'S7'!$E$6:$E$19,"Ambos")+SUMIFS('S8'!$I$6:$I$23,'S8'!$B$6:$B$23,$A39,'S8'!$E$6:$E$23,"Víctor")+SUMIFS('S8'!$I$6:$I$23,'S8'!$B$6:$B$23,$A39,'S8'!$E$6:$E$23,"Ambos")+SUMIFS('S9'!$I$6:$I$15,'S9'!$B$6:$B$15,$A39,'S9'!$E$6:$E$15,"Víctor")+SUMIFS('S9'!$I$6:$I$15,'S9'!$B$6:$B$15,$A39,'S9'!$E$6:$E$15,"Ambos")+SUMIFS('S10'!$I$6:$I$13,'S10'!$B$6:$B$13,$A39,'S10'!$E$6:$E$13,"Víctor")+SUMIFS('S10'!$I$6:$I$13,'S10'!$B$6:$B$13,$A39,'S10'!$E$6:$E$13,"Ambos")+SUMIFS('Holgura'!$I$6:$I$11,'Holgura'!$B$6:$B$11,$A39,'Holgura'!$E$6:$E$11,"Víctor")+SUMIFS('Holgura'!$I$6:$I$11,'Holgura'!$B$6:$B$11,$A39,'Holgura'!$E$6:$E$11,"Ambos")+SUMIFS('Entrega'!$I$6:$I$9,'Entrega'!$B$6:$B$9,$A39,'Entrega'!$E$6:$E$9,"Víctor")+SUMIFS('Entrega'!$I$6:$I$9,'Entrega'!$B$6:$B$9,$A39,'Entrega'!$E$6:$E$9,"Ambos")+SUMIFS('Defensa'!$I$6:$I$10,'Defensa'!$B$6:$B$10,$A39,'Defensa'!$E$6:$E$10,"Víctor")+SUMIFS('Defensa'!$I$6:$I$10,'Defensa'!$B$6:$B$10,$A39,'Defensa'!$E$6:$E$10,"Ambos")</f>
         <v/>
       </c>
       <c r="E39" s="21">
-        <f>SUMIFS('S1'!$I$6:$I$32,'S1'!$B$6:$B$32,$A39,'S1'!$E$6:$E$32,"Diego")+SUMIFS('S1'!$I$6:$I$32,'S1'!$B$6:$B$32,$A39,'S1'!$E$6:$E$32,"Ambos")+SUMIFS('S2'!$I$6:$I$23,'S2'!$B$6:$B$23,$A39,'S2'!$E$6:$E$23,"Diego")+SUMIFS('S2'!$I$6:$I$23,'S2'!$B$6:$B$23,$A39,'S2'!$E$6:$E$23,"Ambos")+SUMIFS('S3'!$I$6:$I$19,'S3'!$B$6:$B$19,$A39,'S3'!$E$6:$E$19,"Diego")+SUMIFS('S3'!$I$6:$I$19,'S3'!$B$6:$B$19,$A39,'S3'!$E$6:$E$19,"Ambos")+SUMIFS('S4'!$I$6:$I$20,'S4'!$B$6:$B$20,$A39,'S4'!$E$6:$E$20,"Diego")+SUMIFS('S4'!$I$6:$I$20,'S4'!$B$6:$B$20,$A39,'S4'!$E$6:$E$20,"Ambos")+SUMIFS('S5'!$I$6:$I$20,'S5'!$B$6:$B$20,$A39,'S5'!$E$6:$E$20,"Diego")+SUMIFS('S5'!$I$6:$I$20,'S5'!$B$6:$B$20,$A39,'S5'!$E$6:$E$20,"Ambos")+SUMIFS('S6'!$I$6:$I$17,'S6'!$B$6:$B$17,$A39,'S6'!$E$6:$E$17,"Diego")+SUMIFS('S6'!$I$6:$I$17,'S6'!$B$6:$B$17,$A39,'S6'!$E$6:$E$17,"Ambos")+SUMIFS('S7'!$I$6:$I$19,'S7'!$B$6:$B$19,$A39,'S7'!$E$6:$E$19,"Diego")+SUMIFS('S7'!$I$6:$I$19,'S7'!$B$6:$B$19,$A39,'S7'!$E$6:$E$19,"Ambos")+SUMIFS('S8'!$I$6:$I$23,'S8'!$B$6:$B$23,$A39,'S8'!$E$6:$E$23,"Diego")+SUMIFS('S8'!$I$6:$I$23,'S8'!$B$6:$B$23,$A39,'S8'!$E$6:$E$23,"Ambos")+SUMIFS('S9'!$I$6:$I$15,'S9'!$B$6:$B$15,$A39,'S9'!$E$6:$E$15,"Diego")+SUMIFS('S9'!$I$6:$I$15,'S9'!$B$6:$B$15,$A39,'S9'!$E$6:$E$15,"Ambos")+SUMIFS('S10'!$I$6:$I$13,'S10'!$B$6:$B$13,$A39,'S10'!$E$6:$E$13,"Diego")+SUMIFS('S10'!$I$6:$I$13,'S10'!$B$6:$B$13,$A39,'S10'!$E$6:$E$13,"Ambos")+SUMIFS('Holgura'!$I$6:$I$11,'Holgura'!$B$6:$B$11,$A39,'Holgura'!$E$6:$E$11,"Diego")+SUMIFS('Holgura'!$I$6:$I$11,'Holgura'!$B$6:$B$11,$A39,'Holgura'!$E$6:$E$11,"Ambos")+SUMIFS('Entrega'!$I$6:$I$9,'Entrega'!$B$6:$B$9,$A39,'Entrega'!$E$6:$E$9,"Diego")+SUMIFS('Entrega'!$I$6:$I$9,'Entrega'!$B$6:$B$9,$A39,'Entrega'!$E$6:$E$9,"Ambos")+SUMIFS('Defensa'!$I$6:$I$10,'Defensa'!$B$6:$B$10,$A39,'Defensa'!$E$6:$E$10,"Diego")+SUMIFS('Defensa'!$I$6:$I$10,'Defensa'!$B$6:$B$10,$A39,'Defensa'!$E$6:$E$10,"Ambos")</f>
+        <f>SUMIFS('S1'!$I$6:$I$32,'S1'!$B$6:$B$32,$A39,'S1'!$E$6:$E$32,"Diego")+SUMIFS('S1'!$I$6:$I$32,'S1'!$B$6:$B$32,$A39,'S1'!$E$6:$E$32,"Ambos")+SUMIFS('S2'!$I$6:$I$23,'S2'!$B$6:$B$23,$A39,'S2'!$E$6:$E$23,"Diego")+SUMIFS('S2'!$I$6:$I$23,'S2'!$B$6:$B$23,$A39,'S2'!$E$6:$E$23,"Ambos")+SUMIFS('S3'!$I$6:$I$24,'S3'!$B$6:$B$24,$A39,'S3'!$E$6:$E$24,"Diego")+SUMIFS('S3'!$I$6:$I$24,'S3'!$B$6:$B$24,$A39,'S3'!$E$6:$E$24,"Ambos")+SUMIFS('S4'!$I$6:$I$22,'S4'!$B$6:$B$22,$A39,'S4'!$E$6:$E$22,"Diego")+SUMIFS('S4'!$I$6:$I$22,'S4'!$B$6:$B$22,$A39,'S4'!$E$6:$E$22,"Ambos")+SUMIFS('S5'!$I$6:$I$20,'S5'!$B$6:$B$20,$A39,'S5'!$E$6:$E$20,"Diego")+SUMIFS('S5'!$I$6:$I$20,'S5'!$B$6:$B$20,$A39,'S5'!$E$6:$E$20,"Ambos")+SUMIFS('S6'!$I$6:$I$17,'S6'!$B$6:$B$17,$A39,'S6'!$E$6:$E$17,"Diego")+SUMIFS('S6'!$I$6:$I$17,'S6'!$B$6:$B$17,$A39,'S6'!$E$6:$E$17,"Ambos")+SUMIFS('S7'!$I$6:$I$19,'S7'!$B$6:$B$19,$A39,'S7'!$E$6:$E$19,"Diego")+SUMIFS('S7'!$I$6:$I$19,'S7'!$B$6:$B$19,$A39,'S7'!$E$6:$E$19,"Ambos")+SUMIFS('S8'!$I$6:$I$23,'S8'!$B$6:$B$23,$A39,'S8'!$E$6:$E$23,"Diego")+SUMIFS('S8'!$I$6:$I$23,'S8'!$B$6:$B$23,$A39,'S8'!$E$6:$E$23,"Ambos")+SUMIFS('S9'!$I$6:$I$15,'S9'!$B$6:$B$15,$A39,'S9'!$E$6:$E$15,"Diego")+SUMIFS('S9'!$I$6:$I$15,'S9'!$B$6:$B$15,$A39,'S9'!$E$6:$E$15,"Ambos")+SUMIFS('S10'!$I$6:$I$13,'S10'!$B$6:$B$13,$A39,'S10'!$E$6:$E$13,"Diego")+SUMIFS('S10'!$I$6:$I$13,'S10'!$B$6:$B$13,$A39,'S10'!$E$6:$E$13,"Ambos")+SUMIFS('Holgura'!$I$6:$I$11,'Holgura'!$B$6:$B$11,$A39,'Holgura'!$E$6:$E$11,"Diego")+SUMIFS('Holgura'!$I$6:$I$11,'Holgura'!$B$6:$B$11,$A39,'Holgura'!$E$6:$E$11,"Ambos")+SUMIFS('Entrega'!$I$6:$I$9,'Entrega'!$B$6:$B$9,$A39,'Entrega'!$E$6:$E$9,"Diego")+SUMIFS('Entrega'!$I$6:$I$9,'Entrega'!$B$6:$B$9,$A39,'Entrega'!$E$6:$E$9,"Ambos")+SUMIFS('Defensa'!$I$6:$I$10,'Defensa'!$B$6:$B$10,$A39,'Defensa'!$E$6:$E$10,"Diego")+SUMIFS('Defensa'!$I$6:$I$10,'Defensa'!$B$6:$B$10,$A39,'Defensa'!$E$6:$E$10,"Ambos")</f>
         <v/>
       </c>
       <c r="F39" s="21">
-        <f>COUNTIFS('S1'!$B$6:$B$32,$A39,'S1'!$E$6:$E$32,"Víctor")+COUNTIFS('S1'!$B$6:$B$32,$A39,'S1'!$E$6:$E$32,"Ambos")+COUNTIFS('S2'!$B$6:$B$23,$A39,'S2'!$E$6:$E$23,"Víctor")+COUNTIFS('S2'!$B$6:$B$23,$A39,'S2'!$E$6:$E$23,"Ambos")+COUNTIFS('S3'!$B$6:$B$19,$A39,'S3'!$E$6:$E$19,"Víctor")+COUNTIFS('S3'!$B$6:$B$19,$A39,'S3'!$E$6:$E$19,"Ambos")+COUNTIFS('S4'!$B$6:$B$20,$A39,'S4'!$E$6:$E$20,"Víctor")+COUNTIFS('S4'!$B$6:$B$20,$A39,'S4'!$E$6:$E$20,"Ambos")+COUNTIFS('S5'!$B$6:$B$20,$A39,'S5'!$E$6:$E$20,"Víctor")+COUNTIFS('S5'!$B$6:$B$20,$A39,'S5'!$E$6:$E$20,"Ambos")+COUNTIFS('S6'!$B$6:$B$17,$A39,'S6'!$E$6:$E$17,"Víctor")+COUNTIFS('S6'!$B$6:$B$17,$A39,'S6'!$E$6:$E$17,"Ambos")+COUNTIFS('S7'!$B$6:$B$19,$A39,'S7'!$E$6:$E$19,"Víctor")+COUNTIFS('S7'!$B$6:$B$19,$A39,'S7'!$E$6:$E$19,"Ambos")+COUNTIFS('S8'!$B$6:$B$23,$A39,'S8'!$E$6:$E$23,"Víctor")+COUNTIFS('S8'!$B$6:$B$23,$A39,'S8'!$E$6:$E$23,"Ambos")+COUNTIFS('S9'!$B$6:$B$15,$A39,'S9'!$E$6:$E$15,"Víctor")+COUNTIFS('S9'!$B$6:$B$15,$A39,'S9'!$E$6:$E$15,"Ambos")+COUNTIFS('S10'!$B$6:$B$13,$A39,'S10'!$E$6:$E$13,"Víctor")+COUNTIFS('S10'!$B$6:$B$13,$A39,'S10'!$E$6:$E$13,"Ambos")+COUNTIFS('Holgura'!$B$6:$B$11,$A39,'Holgura'!$E$6:$E$11,"Víctor")+COUNTIFS('Holgura'!$B$6:$B$11,$A39,'Holgura'!$E$6:$E$11,"Ambos")+COUNTIFS('Entrega'!$B$6:$B$9,$A39,'Entrega'!$E$6:$E$9,"Víctor")+COUNTIFS('Entrega'!$B$6:$B$9,$A39,'Entrega'!$E$6:$E$9,"Ambos")+COUNTIFS('Defensa'!$B$6:$B$10,$A39,'Defensa'!$E$6:$E$10,"Víctor")+COUNTIFS('Defensa'!$B$6:$B$10,$A39,'Defensa'!$E$6:$E$10,"Ambos")</f>
+        <f>COUNTIFS('S1'!$B$6:$B$32,$A39,'S1'!$E$6:$E$32,"Víctor")+COUNTIFS('S1'!$B$6:$B$32,$A39,'S1'!$E$6:$E$32,"Ambos")+COUNTIFS('S2'!$B$6:$B$23,$A39,'S2'!$E$6:$E$23,"Víctor")+COUNTIFS('S2'!$B$6:$B$23,$A39,'S2'!$E$6:$E$23,"Ambos")+COUNTIFS('S3'!$B$6:$B$24,$A39,'S3'!$E$6:$E$24,"Víctor")+COUNTIFS('S3'!$B$6:$B$24,$A39,'S3'!$E$6:$E$24,"Ambos")+COUNTIFS('S4'!$B$6:$B$22,$A39,'S4'!$E$6:$E$22,"Víctor")+COUNTIFS('S4'!$B$6:$B$22,$A39,'S4'!$E$6:$E$22,"Ambos")+COUNTIFS('S5'!$B$6:$B$20,$A39,'S5'!$E$6:$E$20,"Víctor")+COUNTIFS('S5'!$B$6:$B$20,$A39,'S5'!$E$6:$E$20,"Ambos")+COUNTIFS('S6'!$B$6:$B$17,$A39,'S6'!$E$6:$E$17,"Víctor")+COUNTIFS('S6'!$B$6:$B$17,$A39,'S6'!$E$6:$E$17,"Ambos")+COUNTIFS('S7'!$B$6:$B$19,$A39,'S7'!$E$6:$E$19,"Víctor")+COUNTIFS('S7'!$B$6:$B$19,$A39,'S7'!$E$6:$E$19,"Ambos")+COUNTIFS('S8'!$B$6:$B$23,$A39,'S8'!$E$6:$E$23,"Víctor")+COUNTIFS('S8'!$B$6:$B$23,$A39,'S8'!$E$6:$E$23,"Ambos")+COUNTIFS('S9'!$B$6:$B$15,$A39,'S9'!$E$6:$E$15,"Víctor")+COUNTIFS('S9'!$B$6:$B$15,$A39,'S9'!$E$6:$E$15,"Ambos")+COUNTIFS('S10'!$B$6:$B$13,$A39,'S10'!$E$6:$E$13,"Víctor")+COUNTIFS('S10'!$B$6:$B$13,$A39,'S10'!$E$6:$E$13,"Ambos")+COUNTIFS('Holgura'!$B$6:$B$11,$A39,'Holgura'!$E$6:$E$11,"Víctor")+COUNTIFS('Holgura'!$B$6:$B$11,$A39,'Holgura'!$E$6:$E$11,"Ambos")+COUNTIFS('Entrega'!$B$6:$B$9,$A39,'Entrega'!$E$6:$E$9,"Víctor")+COUNTIFS('Entrega'!$B$6:$B$9,$A39,'Entrega'!$E$6:$E$9,"Ambos")+COUNTIFS('Defensa'!$B$6:$B$10,$A39,'Defensa'!$E$6:$E$10,"Víctor")+COUNTIFS('Defensa'!$B$6:$B$10,$A39,'Defensa'!$E$6:$E$10,"Ambos")</f>
         <v/>
       </c>
       <c r="G39" s="21">
-        <f>COUNTIFS('S1'!$B$6:$B$32,$A39,'S1'!$E$6:$E$32,"Diego")+COUNTIFS('S1'!$B$6:$B$32,$A39,'S1'!$E$6:$E$32,"Ambos")+COUNTIFS('S2'!$B$6:$B$23,$A39,'S2'!$E$6:$E$23,"Diego")+COUNTIFS('S2'!$B$6:$B$23,$A39,'S2'!$E$6:$E$23,"Ambos")+COUNTIFS('S3'!$B$6:$B$19,$A39,'S3'!$E$6:$E$19,"Diego")+COUNTIFS('S3'!$B$6:$B$19,$A39,'S3'!$E$6:$E$19,"Ambos")+COUNTIFS('S4'!$B$6:$B$20,$A39,'S4'!$E$6:$E$20,"Diego")+COUNTIFS('S4'!$B$6:$B$20,$A39,'S4'!$E$6:$E$20,"Ambos")+COUNTIFS('S5'!$B$6:$B$20,$A39,'S5'!$E$6:$E$20,"Diego")+COUNTIFS('S5'!$B$6:$B$20,$A39,'S5'!$E$6:$E$20,"Ambos")+COUNTIFS('S6'!$B$6:$B$17,$A39,'S6'!$E$6:$E$17,"Diego")+COUNTIFS('S6'!$B$6:$B$17,$A39,'S6'!$E$6:$E$17,"Ambos")+COUNTIFS('S7'!$B$6:$B$19,$A39,'S7'!$E$6:$E$19,"Diego")+COUNTIFS('S7'!$B$6:$B$19,$A39,'S7'!$E$6:$E$19,"Ambos")+COUNTIFS('S8'!$B$6:$B$23,$A39,'S8'!$E$6:$E$23,"Diego")+COUNTIFS('S8'!$B$6:$B$23,$A39,'S8'!$E$6:$E$23,"Ambos")+COUNTIFS('S9'!$B$6:$B$15,$A39,'S9'!$E$6:$E$15,"Diego")+COUNTIFS('S9'!$B$6:$B$15,$A39,'S9'!$E$6:$E$15,"Ambos")+COUNTIFS('S10'!$B$6:$B$13,$A39,'S10'!$E$6:$E$13,"Diego")+COUNTIFS('S10'!$B$6:$B$13,$A39,'S10'!$E$6:$E$13,"Ambos")+COUNTIFS('Holgura'!$B$6:$B$11,$A39,'Holgura'!$E$6:$E$11,"Diego")+COUNTIFS('Holgura'!$B$6:$B$11,$A39,'Holgura'!$E$6:$E$11,"Ambos")+COUNTIFS('Entrega'!$B$6:$B$9,$A39,'Entrega'!$E$6:$E$9,"Diego")+COUNTIFS('Entrega'!$B$6:$B$9,$A39,'Entrega'!$E$6:$E$9,"Ambos")+COUNTIFS('Defensa'!$B$6:$B$10,$A39,'Defensa'!$E$6:$E$10,"Diego")+COUNTIFS('Defensa'!$B$6:$B$10,$A39,'Defensa'!$E$6:$E$10,"Ambos")</f>
+        <f>COUNTIFS('S1'!$B$6:$B$32,$A39,'S1'!$E$6:$E$32,"Diego")+COUNTIFS('S1'!$B$6:$B$32,$A39,'S1'!$E$6:$E$32,"Ambos")+COUNTIFS('S2'!$B$6:$B$23,$A39,'S2'!$E$6:$E$23,"Diego")+COUNTIFS('S2'!$B$6:$B$23,$A39,'S2'!$E$6:$E$23,"Ambos")+COUNTIFS('S3'!$B$6:$B$24,$A39,'S3'!$E$6:$E$24,"Diego")+COUNTIFS('S3'!$B$6:$B$24,$A39,'S3'!$E$6:$E$24,"Ambos")+COUNTIFS('S4'!$B$6:$B$22,$A39,'S4'!$E$6:$E$22,"Diego")+COUNTIFS('S4'!$B$6:$B$22,$A39,'S4'!$E$6:$E$22,"Ambos")+COUNTIFS('S5'!$B$6:$B$20,$A39,'S5'!$E$6:$E$20,"Diego")+COUNTIFS('S5'!$B$6:$B$20,$A39,'S5'!$E$6:$E$20,"Ambos")+COUNTIFS('S6'!$B$6:$B$17,$A39,'S6'!$E$6:$E$17,"Diego")+COUNTIFS('S6'!$B$6:$B$17,$A39,'S6'!$E$6:$E$17,"Ambos")+COUNTIFS('S7'!$B$6:$B$19,$A39,'S7'!$E$6:$E$19,"Diego")+COUNTIFS('S7'!$B$6:$B$19,$A39,'S7'!$E$6:$E$19,"Ambos")+COUNTIFS('S8'!$B$6:$B$23,$A39,'S8'!$E$6:$E$23,"Diego")+COUNTIFS('S8'!$B$6:$B$23,$A39,'S8'!$E$6:$E$23,"Ambos")+COUNTIFS('S9'!$B$6:$B$15,$A39,'S9'!$E$6:$E$15,"Diego")+COUNTIFS('S9'!$B$6:$B$15,$A39,'S9'!$E$6:$E$15,"Ambos")+COUNTIFS('S10'!$B$6:$B$13,$A39,'S10'!$E$6:$E$13,"Diego")+COUNTIFS('S10'!$B$6:$B$13,$A39,'S10'!$E$6:$E$13,"Ambos")+COUNTIFS('Holgura'!$B$6:$B$11,$A39,'Holgura'!$E$6:$E$11,"Diego")+COUNTIFS('Holgura'!$B$6:$B$11,$A39,'Holgura'!$E$6:$E$11,"Ambos")+COUNTIFS('Entrega'!$B$6:$B$9,$A39,'Entrega'!$E$6:$E$9,"Diego")+COUNTIFS('Entrega'!$B$6:$B$9,$A39,'Entrega'!$E$6:$E$9,"Ambos")+COUNTIFS('Defensa'!$B$6:$B$10,$A39,'Defensa'!$E$6:$E$10,"Diego")+COUNTIFS('Defensa'!$B$6:$B$10,$A39,'Defensa'!$E$6:$E$10,"Ambos")</f>
         <v/>
       </c>
     </row>
@@ -9695,19 +9716,19 @@
         <v/>
       </c>
       <c r="D40" s="21">
-        <f>SUMIFS('S1'!$I$6:$I$32,'S1'!$B$6:$B$32,$A40,'S1'!$E$6:$E$32,"Víctor")+SUMIFS('S1'!$I$6:$I$32,'S1'!$B$6:$B$32,$A40,'S1'!$E$6:$E$32,"Ambos")+SUMIFS('S2'!$I$6:$I$23,'S2'!$B$6:$B$23,$A40,'S2'!$E$6:$E$23,"Víctor")+SUMIFS('S2'!$I$6:$I$23,'S2'!$B$6:$B$23,$A40,'S2'!$E$6:$E$23,"Ambos")+SUMIFS('S3'!$I$6:$I$19,'S3'!$B$6:$B$19,$A40,'S3'!$E$6:$E$19,"Víctor")+SUMIFS('S3'!$I$6:$I$19,'S3'!$B$6:$B$19,$A40,'S3'!$E$6:$E$19,"Ambos")+SUMIFS('S4'!$I$6:$I$20,'S4'!$B$6:$B$20,$A40,'S4'!$E$6:$E$20,"Víctor")+SUMIFS('S4'!$I$6:$I$20,'S4'!$B$6:$B$20,$A40,'S4'!$E$6:$E$20,"Ambos")+SUMIFS('S5'!$I$6:$I$20,'S5'!$B$6:$B$20,$A40,'S5'!$E$6:$E$20,"Víctor")+SUMIFS('S5'!$I$6:$I$20,'S5'!$B$6:$B$20,$A40,'S5'!$E$6:$E$20,"Ambos")+SUMIFS('S6'!$I$6:$I$17,'S6'!$B$6:$B$17,$A40,'S6'!$E$6:$E$17,"Víctor")+SUMIFS('S6'!$I$6:$I$17,'S6'!$B$6:$B$17,$A40,'S6'!$E$6:$E$17,"Ambos")+SUMIFS('S7'!$I$6:$I$19,'S7'!$B$6:$B$19,$A40,'S7'!$E$6:$E$19,"Víctor")+SUMIFS('S7'!$I$6:$I$19,'S7'!$B$6:$B$19,$A40,'S7'!$E$6:$E$19,"Ambos")+SUMIFS('S8'!$I$6:$I$23,'S8'!$B$6:$B$23,$A40,'S8'!$E$6:$E$23,"Víctor")+SUMIFS('S8'!$I$6:$I$23,'S8'!$B$6:$B$23,$A40,'S8'!$E$6:$E$23,"Ambos")+SUMIFS('S9'!$I$6:$I$15,'S9'!$B$6:$B$15,$A40,'S9'!$E$6:$E$15,"Víctor")+SUMIFS('S9'!$I$6:$I$15,'S9'!$B$6:$B$15,$A40,'S9'!$E$6:$E$15,"Ambos")+SUMIFS('S10'!$I$6:$I$13,'S10'!$B$6:$B$13,$A40,'S10'!$E$6:$E$13,"Víctor")+SUMIFS('S10'!$I$6:$I$13,'S10'!$B$6:$B$13,$A40,'S10'!$E$6:$E$13,"Ambos")+SUMIFS('Holgura'!$I$6:$I$11,'Holgura'!$B$6:$B$11,$A40,'Holgura'!$E$6:$E$11,"Víctor")+SUMIFS('Holgura'!$I$6:$I$11,'Holgura'!$B$6:$B$11,$A40,'Holgura'!$E$6:$E$11,"Ambos")+SUMIFS('Entrega'!$I$6:$I$9,'Entrega'!$B$6:$B$9,$A40,'Entrega'!$E$6:$E$9,"Víctor")+SUMIFS('Entrega'!$I$6:$I$9,'Entrega'!$B$6:$B$9,$A40,'Entrega'!$E$6:$E$9,"Ambos")+SUMIFS('Defensa'!$I$6:$I$10,'Defensa'!$B$6:$B$10,$A40,'Defensa'!$E$6:$E$10,"Víctor")+SUMIFS('Defensa'!$I$6:$I$10,'Defensa'!$B$6:$B$10,$A40,'Defensa'!$E$6:$E$10,"Ambos")</f>
+        <f>SUMIFS('S1'!$I$6:$I$32,'S1'!$B$6:$B$32,$A40,'S1'!$E$6:$E$32,"Víctor")+SUMIFS('S1'!$I$6:$I$32,'S1'!$B$6:$B$32,$A40,'S1'!$E$6:$E$32,"Ambos")+SUMIFS('S2'!$I$6:$I$23,'S2'!$B$6:$B$23,$A40,'S2'!$E$6:$E$23,"Víctor")+SUMIFS('S2'!$I$6:$I$23,'S2'!$B$6:$B$23,$A40,'S2'!$E$6:$E$23,"Ambos")+SUMIFS('S3'!$I$6:$I$24,'S3'!$B$6:$B$24,$A40,'S3'!$E$6:$E$24,"Víctor")+SUMIFS('S3'!$I$6:$I$24,'S3'!$B$6:$B$24,$A40,'S3'!$E$6:$E$24,"Ambos")+SUMIFS('S4'!$I$6:$I$22,'S4'!$B$6:$B$22,$A40,'S4'!$E$6:$E$22,"Víctor")+SUMIFS('S4'!$I$6:$I$22,'S4'!$B$6:$B$22,$A40,'S4'!$E$6:$E$22,"Ambos")+SUMIFS('S5'!$I$6:$I$20,'S5'!$B$6:$B$20,$A40,'S5'!$E$6:$E$20,"Víctor")+SUMIFS('S5'!$I$6:$I$20,'S5'!$B$6:$B$20,$A40,'S5'!$E$6:$E$20,"Ambos")+SUMIFS('S6'!$I$6:$I$17,'S6'!$B$6:$B$17,$A40,'S6'!$E$6:$E$17,"Víctor")+SUMIFS('S6'!$I$6:$I$17,'S6'!$B$6:$B$17,$A40,'S6'!$E$6:$E$17,"Ambos")+SUMIFS('S7'!$I$6:$I$19,'S7'!$B$6:$B$19,$A40,'S7'!$E$6:$E$19,"Víctor")+SUMIFS('S7'!$I$6:$I$19,'S7'!$B$6:$B$19,$A40,'S7'!$E$6:$E$19,"Ambos")+SUMIFS('S8'!$I$6:$I$23,'S8'!$B$6:$B$23,$A40,'S8'!$E$6:$E$23,"Víctor")+SUMIFS('S8'!$I$6:$I$23,'S8'!$B$6:$B$23,$A40,'S8'!$E$6:$E$23,"Ambos")+SUMIFS('S9'!$I$6:$I$15,'S9'!$B$6:$B$15,$A40,'S9'!$E$6:$E$15,"Víctor")+SUMIFS('S9'!$I$6:$I$15,'S9'!$B$6:$B$15,$A40,'S9'!$E$6:$E$15,"Ambos")+SUMIFS('S10'!$I$6:$I$13,'S10'!$B$6:$B$13,$A40,'S10'!$E$6:$E$13,"Víctor")+SUMIFS('S10'!$I$6:$I$13,'S10'!$B$6:$B$13,$A40,'S10'!$E$6:$E$13,"Ambos")+SUMIFS('Holgura'!$I$6:$I$11,'Holgura'!$B$6:$B$11,$A40,'Holgura'!$E$6:$E$11,"Víctor")+SUMIFS('Holgura'!$I$6:$I$11,'Holgura'!$B$6:$B$11,$A40,'Holgura'!$E$6:$E$11,"Ambos")+SUMIFS('Entrega'!$I$6:$I$9,'Entrega'!$B$6:$B$9,$A40,'Entrega'!$E$6:$E$9,"Víctor")+SUMIFS('Entrega'!$I$6:$I$9,'Entrega'!$B$6:$B$9,$A40,'Entrega'!$E$6:$E$9,"Ambos")+SUMIFS('Defensa'!$I$6:$I$10,'Defensa'!$B$6:$B$10,$A40,'Defensa'!$E$6:$E$10,"Víctor")+SUMIFS('Defensa'!$I$6:$I$10,'Defensa'!$B$6:$B$10,$A40,'Defensa'!$E$6:$E$10,"Ambos")</f>
         <v/>
       </c>
       <c r="E40" s="21">
-        <f>SUMIFS('S1'!$I$6:$I$32,'S1'!$B$6:$B$32,$A40,'S1'!$E$6:$E$32,"Diego")+SUMIFS('S1'!$I$6:$I$32,'S1'!$B$6:$B$32,$A40,'S1'!$E$6:$E$32,"Ambos")+SUMIFS('S2'!$I$6:$I$23,'S2'!$B$6:$B$23,$A40,'S2'!$E$6:$E$23,"Diego")+SUMIFS('S2'!$I$6:$I$23,'S2'!$B$6:$B$23,$A40,'S2'!$E$6:$E$23,"Ambos")+SUMIFS('S3'!$I$6:$I$19,'S3'!$B$6:$B$19,$A40,'S3'!$E$6:$E$19,"Diego")+SUMIFS('S3'!$I$6:$I$19,'S3'!$B$6:$B$19,$A40,'S3'!$E$6:$E$19,"Ambos")+SUMIFS('S4'!$I$6:$I$20,'S4'!$B$6:$B$20,$A40,'S4'!$E$6:$E$20,"Diego")+SUMIFS('S4'!$I$6:$I$20,'S4'!$B$6:$B$20,$A40,'S4'!$E$6:$E$20,"Ambos")+SUMIFS('S5'!$I$6:$I$20,'S5'!$B$6:$B$20,$A40,'S5'!$E$6:$E$20,"Diego")+SUMIFS('S5'!$I$6:$I$20,'S5'!$B$6:$B$20,$A40,'S5'!$E$6:$E$20,"Ambos")+SUMIFS('S6'!$I$6:$I$17,'S6'!$B$6:$B$17,$A40,'S6'!$E$6:$E$17,"Diego")+SUMIFS('S6'!$I$6:$I$17,'S6'!$B$6:$B$17,$A40,'S6'!$E$6:$E$17,"Ambos")+SUMIFS('S7'!$I$6:$I$19,'S7'!$B$6:$B$19,$A40,'S7'!$E$6:$E$19,"Diego")+SUMIFS('S7'!$I$6:$I$19,'S7'!$B$6:$B$19,$A40,'S7'!$E$6:$E$19,"Ambos")+SUMIFS('S8'!$I$6:$I$23,'S8'!$B$6:$B$23,$A40,'S8'!$E$6:$E$23,"Diego")+SUMIFS('S8'!$I$6:$I$23,'S8'!$B$6:$B$23,$A40,'S8'!$E$6:$E$23,"Ambos")+SUMIFS('S9'!$I$6:$I$15,'S9'!$B$6:$B$15,$A40,'S9'!$E$6:$E$15,"Diego")+SUMIFS('S9'!$I$6:$I$15,'S9'!$B$6:$B$15,$A40,'S9'!$E$6:$E$15,"Ambos")+SUMIFS('S10'!$I$6:$I$13,'S10'!$B$6:$B$13,$A40,'S10'!$E$6:$E$13,"Diego")+SUMIFS('S10'!$I$6:$I$13,'S10'!$B$6:$B$13,$A40,'S10'!$E$6:$E$13,"Ambos")+SUMIFS('Holgura'!$I$6:$I$11,'Holgura'!$B$6:$B$11,$A40,'Holgura'!$E$6:$E$11,"Diego")+SUMIFS('Holgura'!$I$6:$I$11,'Holgura'!$B$6:$B$11,$A40,'Holgura'!$E$6:$E$11,"Ambos")+SUMIFS('Entrega'!$I$6:$I$9,'Entrega'!$B$6:$B$9,$A40,'Entrega'!$E$6:$E$9,"Diego")+SUMIFS('Entrega'!$I$6:$I$9,'Entrega'!$B$6:$B$9,$A40,'Entrega'!$E$6:$E$9,"Ambos")+SUMIFS('Defensa'!$I$6:$I$10,'Defensa'!$B$6:$B$10,$A40,'Defensa'!$E$6:$E$10,"Diego")+SUMIFS('Defensa'!$I$6:$I$10,'Defensa'!$B$6:$B$10,$A40,'Defensa'!$E$6:$E$10,"Ambos")</f>
+        <f>SUMIFS('S1'!$I$6:$I$32,'S1'!$B$6:$B$32,$A40,'S1'!$E$6:$E$32,"Diego")+SUMIFS('S1'!$I$6:$I$32,'S1'!$B$6:$B$32,$A40,'S1'!$E$6:$E$32,"Ambos")+SUMIFS('S2'!$I$6:$I$23,'S2'!$B$6:$B$23,$A40,'S2'!$E$6:$E$23,"Diego")+SUMIFS('S2'!$I$6:$I$23,'S2'!$B$6:$B$23,$A40,'S2'!$E$6:$E$23,"Ambos")+SUMIFS('S3'!$I$6:$I$24,'S3'!$B$6:$B$24,$A40,'S3'!$E$6:$E$24,"Diego")+SUMIFS('S3'!$I$6:$I$24,'S3'!$B$6:$B$24,$A40,'S3'!$E$6:$E$24,"Ambos")+SUMIFS('S4'!$I$6:$I$22,'S4'!$B$6:$B$22,$A40,'S4'!$E$6:$E$22,"Diego")+SUMIFS('S4'!$I$6:$I$22,'S4'!$B$6:$B$22,$A40,'S4'!$E$6:$E$22,"Ambos")+SUMIFS('S5'!$I$6:$I$20,'S5'!$B$6:$B$20,$A40,'S5'!$E$6:$E$20,"Diego")+SUMIFS('S5'!$I$6:$I$20,'S5'!$B$6:$B$20,$A40,'S5'!$E$6:$E$20,"Ambos")+SUMIFS('S6'!$I$6:$I$17,'S6'!$B$6:$B$17,$A40,'S6'!$E$6:$E$17,"Diego")+SUMIFS('S6'!$I$6:$I$17,'S6'!$B$6:$B$17,$A40,'S6'!$E$6:$E$17,"Ambos")+SUMIFS('S7'!$I$6:$I$19,'S7'!$B$6:$B$19,$A40,'S7'!$E$6:$E$19,"Diego")+SUMIFS('S7'!$I$6:$I$19,'S7'!$B$6:$B$19,$A40,'S7'!$E$6:$E$19,"Ambos")+SUMIFS('S8'!$I$6:$I$23,'S8'!$B$6:$B$23,$A40,'S8'!$E$6:$E$23,"Diego")+SUMIFS('S8'!$I$6:$I$23,'S8'!$B$6:$B$23,$A40,'S8'!$E$6:$E$23,"Ambos")+SUMIFS('S9'!$I$6:$I$15,'S9'!$B$6:$B$15,$A40,'S9'!$E$6:$E$15,"Diego")+SUMIFS('S9'!$I$6:$I$15,'S9'!$B$6:$B$15,$A40,'S9'!$E$6:$E$15,"Ambos")+SUMIFS('S10'!$I$6:$I$13,'S10'!$B$6:$B$13,$A40,'S10'!$E$6:$E$13,"Diego")+SUMIFS('S10'!$I$6:$I$13,'S10'!$B$6:$B$13,$A40,'S10'!$E$6:$E$13,"Ambos")+SUMIFS('Holgura'!$I$6:$I$11,'Holgura'!$B$6:$B$11,$A40,'Holgura'!$E$6:$E$11,"Diego")+SUMIFS('Holgura'!$I$6:$I$11,'Holgura'!$B$6:$B$11,$A40,'Holgura'!$E$6:$E$11,"Ambos")+SUMIFS('Entrega'!$I$6:$I$9,'Entrega'!$B$6:$B$9,$A40,'Entrega'!$E$6:$E$9,"Diego")+SUMIFS('Entrega'!$I$6:$I$9,'Entrega'!$B$6:$B$9,$A40,'Entrega'!$E$6:$E$9,"Ambos")+SUMIFS('Defensa'!$I$6:$I$10,'Defensa'!$B$6:$B$10,$A40,'Defensa'!$E$6:$E$10,"Diego")+SUMIFS('Defensa'!$I$6:$I$10,'Defensa'!$B$6:$B$10,$A40,'Defensa'!$E$6:$E$10,"Ambos")</f>
         <v/>
       </c>
       <c r="F40" s="21">
-        <f>COUNTIFS('S1'!$B$6:$B$32,$A40,'S1'!$E$6:$E$32,"Víctor")+COUNTIFS('S1'!$B$6:$B$32,$A40,'S1'!$E$6:$E$32,"Ambos")+COUNTIFS('S2'!$B$6:$B$23,$A40,'S2'!$E$6:$E$23,"Víctor")+COUNTIFS('S2'!$B$6:$B$23,$A40,'S2'!$E$6:$E$23,"Ambos")+COUNTIFS('S3'!$B$6:$B$19,$A40,'S3'!$E$6:$E$19,"Víctor")+COUNTIFS('S3'!$B$6:$B$19,$A40,'S3'!$E$6:$E$19,"Ambos")+COUNTIFS('S4'!$B$6:$B$20,$A40,'S4'!$E$6:$E$20,"Víctor")+COUNTIFS('S4'!$B$6:$B$20,$A40,'S4'!$E$6:$E$20,"Ambos")+COUNTIFS('S5'!$B$6:$B$20,$A40,'S5'!$E$6:$E$20,"Víctor")+COUNTIFS('S5'!$B$6:$B$20,$A40,'S5'!$E$6:$E$20,"Ambos")+COUNTIFS('S6'!$B$6:$B$17,$A40,'S6'!$E$6:$E$17,"Víctor")+COUNTIFS('S6'!$B$6:$B$17,$A40,'S6'!$E$6:$E$17,"Ambos")+COUNTIFS('S7'!$B$6:$B$19,$A40,'S7'!$E$6:$E$19,"Víctor")+COUNTIFS('S7'!$B$6:$B$19,$A40,'S7'!$E$6:$E$19,"Ambos")+COUNTIFS('S8'!$B$6:$B$23,$A40,'S8'!$E$6:$E$23,"Víctor")+COUNTIFS('S8'!$B$6:$B$23,$A40,'S8'!$E$6:$E$23,"Ambos")+COUNTIFS('S9'!$B$6:$B$15,$A40,'S9'!$E$6:$E$15,"Víctor")+COUNTIFS('S9'!$B$6:$B$15,$A40,'S9'!$E$6:$E$15,"Ambos")+COUNTIFS('S10'!$B$6:$B$13,$A40,'S10'!$E$6:$E$13,"Víctor")+COUNTIFS('S10'!$B$6:$B$13,$A40,'S10'!$E$6:$E$13,"Ambos")+COUNTIFS('Holgura'!$B$6:$B$11,$A40,'Holgura'!$E$6:$E$11,"Víctor")+COUNTIFS('Holgura'!$B$6:$B$11,$A40,'Holgura'!$E$6:$E$11,"Ambos")+COUNTIFS('Entrega'!$B$6:$B$9,$A40,'Entrega'!$E$6:$E$9,"Víctor")+COUNTIFS('Entrega'!$B$6:$B$9,$A40,'Entrega'!$E$6:$E$9,"Ambos")+COUNTIFS('Defensa'!$B$6:$B$10,$A40,'Defensa'!$E$6:$E$10,"Víctor")+COUNTIFS('Defensa'!$B$6:$B$10,$A40,'Defensa'!$E$6:$E$10,"Ambos")</f>
+        <f>COUNTIFS('S1'!$B$6:$B$32,$A40,'S1'!$E$6:$E$32,"Víctor")+COUNTIFS('S1'!$B$6:$B$32,$A40,'S1'!$E$6:$E$32,"Ambos")+COUNTIFS('S2'!$B$6:$B$23,$A40,'S2'!$E$6:$E$23,"Víctor")+COUNTIFS('S2'!$B$6:$B$23,$A40,'S2'!$E$6:$E$23,"Ambos")+COUNTIFS('S3'!$B$6:$B$24,$A40,'S3'!$E$6:$E$24,"Víctor")+COUNTIFS('S3'!$B$6:$B$24,$A40,'S3'!$E$6:$E$24,"Ambos")+COUNTIFS('S4'!$B$6:$B$22,$A40,'S4'!$E$6:$E$22,"Víctor")+COUNTIFS('S4'!$B$6:$B$22,$A40,'S4'!$E$6:$E$22,"Ambos")+COUNTIFS('S5'!$B$6:$B$20,$A40,'S5'!$E$6:$E$20,"Víctor")+COUNTIFS('S5'!$B$6:$B$20,$A40,'S5'!$E$6:$E$20,"Ambos")+COUNTIFS('S6'!$B$6:$B$17,$A40,'S6'!$E$6:$E$17,"Víctor")+COUNTIFS('S6'!$B$6:$B$17,$A40,'S6'!$E$6:$E$17,"Ambos")+COUNTIFS('S7'!$B$6:$B$19,$A40,'S7'!$E$6:$E$19,"Víctor")+COUNTIFS('S7'!$B$6:$B$19,$A40,'S7'!$E$6:$E$19,"Ambos")+COUNTIFS('S8'!$B$6:$B$23,$A40,'S8'!$E$6:$E$23,"Víctor")+COUNTIFS('S8'!$B$6:$B$23,$A40,'S8'!$E$6:$E$23,"Ambos")+COUNTIFS('S9'!$B$6:$B$15,$A40,'S9'!$E$6:$E$15,"Víctor")+COUNTIFS('S9'!$B$6:$B$15,$A40,'S9'!$E$6:$E$15,"Ambos")+COUNTIFS('S10'!$B$6:$B$13,$A40,'S10'!$E$6:$E$13,"Víctor")+COUNTIFS('S10'!$B$6:$B$13,$A40,'S10'!$E$6:$E$13,"Ambos")+COUNTIFS('Holgura'!$B$6:$B$11,$A40,'Holgura'!$E$6:$E$11,"Víctor")+COUNTIFS('Holgura'!$B$6:$B$11,$A40,'Holgura'!$E$6:$E$11,"Ambos")+COUNTIFS('Entrega'!$B$6:$B$9,$A40,'Entrega'!$E$6:$E$9,"Víctor")+COUNTIFS('Entrega'!$B$6:$B$9,$A40,'Entrega'!$E$6:$E$9,"Ambos")+COUNTIFS('Defensa'!$B$6:$B$10,$A40,'Defensa'!$E$6:$E$10,"Víctor")+COUNTIFS('Defensa'!$B$6:$B$10,$A40,'Defensa'!$E$6:$E$10,"Ambos")</f>
         <v/>
       </c>
       <c r="G40" s="21">
-        <f>COUNTIFS('S1'!$B$6:$B$32,$A40,'S1'!$E$6:$E$32,"Diego")+COUNTIFS('S1'!$B$6:$B$32,$A40,'S1'!$E$6:$E$32,"Ambos")+COUNTIFS('S2'!$B$6:$B$23,$A40,'S2'!$E$6:$E$23,"Diego")+COUNTIFS('S2'!$B$6:$B$23,$A40,'S2'!$E$6:$E$23,"Ambos")+COUNTIFS('S3'!$B$6:$B$19,$A40,'S3'!$E$6:$E$19,"Diego")+COUNTIFS('S3'!$B$6:$B$19,$A40,'S3'!$E$6:$E$19,"Ambos")+COUNTIFS('S4'!$B$6:$B$20,$A40,'S4'!$E$6:$E$20,"Diego")+COUNTIFS('S4'!$B$6:$B$20,$A40,'S4'!$E$6:$E$20,"Ambos")+COUNTIFS('S5'!$B$6:$B$20,$A40,'S5'!$E$6:$E$20,"Diego")+COUNTIFS('S5'!$B$6:$B$20,$A40,'S5'!$E$6:$E$20,"Ambos")+COUNTIFS('S6'!$B$6:$B$17,$A40,'S6'!$E$6:$E$17,"Diego")+COUNTIFS('S6'!$B$6:$B$17,$A40,'S6'!$E$6:$E$17,"Ambos")+COUNTIFS('S7'!$B$6:$B$19,$A40,'S7'!$E$6:$E$19,"Diego")+COUNTIFS('S7'!$B$6:$B$19,$A40,'S7'!$E$6:$E$19,"Ambos")+COUNTIFS('S8'!$B$6:$B$23,$A40,'S8'!$E$6:$E$23,"Diego")+COUNTIFS('S8'!$B$6:$B$23,$A40,'S8'!$E$6:$E$23,"Ambos")+COUNTIFS('S9'!$B$6:$B$15,$A40,'S9'!$E$6:$E$15,"Diego")+COUNTIFS('S9'!$B$6:$B$15,$A40,'S9'!$E$6:$E$15,"Ambos")+COUNTIFS('S10'!$B$6:$B$13,$A40,'S10'!$E$6:$E$13,"Diego")+COUNTIFS('S10'!$B$6:$B$13,$A40,'S10'!$E$6:$E$13,"Ambos")+COUNTIFS('Holgura'!$B$6:$B$11,$A40,'Holgura'!$E$6:$E$11,"Diego")+COUNTIFS('Holgura'!$B$6:$B$11,$A40,'Holgura'!$E$6:$E$11,"Ambos")+COUNTIFS('Entrega'!$B$6:$B$9,$A40,'Entrega'!$E$6:$E$9,"Diego")+COUNTIFS('Entrega'!$B$6:$B$9,$A40,'Entrega'!$E$6:$E$9,"Ambos")+COUNTIFS('Defensa'!$B$6:$B$10,$A40,'Defensa'!$E$6:$E$10,"Diego")+COUNTIFS('Defensa'!$B$6:$B$10,$A40,'Defensa'!$E$6:$E$10,"Ambos")</f>
+        <f>COUNTIFS('S1'!$B$6:$B$32,$A40,'S1'!$E$6:$E$32,"Diego")+COUNTIFS('S1'!$B$6:$B$32,$A40,'S1'!$E$6:$E$32,"Ambos")+COUNTIFS('S2'!$B$6:$B$23,$A40,'S2'!$E$6:$E$23,"Diego")+COUNTIFS('S2'!$B$6:$B$23,$A40,'S2'!$E$6:$E$23,"Ambos")+COUNTIFS('S3'!$B$6:$B$24,$A40,'S3'!$E$6:$E$24,"Diego")+COUNTIFS('S3'!$B$6:$B$24,$A40,'S3'!$E$6:$E$24,"Ambos")+COUNTIFS('S4'!$B$6:$B$22,$A40,'S4'!$E$6:$E$22,"Diego")+COUNTIFS('S4'!$B$6:$B$22,$A40,'S4'!$E$6:$E$22,"Ambos")+COUNTIFS('S5'!$B$6:$B$20,$A40,'S5'!$E$6:$E$20,"Diego")+COUNTIFS('S5'!$B$6:$B$20,$A40,'S5'!$E$6:$E$20,"Ambos")+COUNTIFS('S6'!$B$6:$B$17,$A40,'S6'!$E$6:$E$17,"Diego")+COUNTIFS('S6'!$B$6:$B$17,$A40,'S6'!$E$6:$E$17,"Ambos")+COUNTIFS('S7'!$B$6:$B$19,$A40,'S7'!$E$6:$E$19,"Diego")+COUNTIFS('S7'!$B$6:$B$19,$A40,'S7'!$E$6:$E$19,"Ambos")+COUNTIFS('S8'!$B$6:$B$23,$A40,'S8'!$E$6:$E$23,"Diego")+COUNTIFS('S8'!$B$6:$B$23,$A40,'S8'!$E$6:$E$23,"Ambos")+COUNTIFS('S9'!$B$6:$B$15,$A40,'S9'!$E$6:$E$15,"Diego")+COUNTIFS('S9'!$B$6:$B$15,$A40,'S9'!$E$6:$E$15,"Ambos")+COUNTIFS('S10'!$B$6:$B$13,$A40,'S10'!$E$6:$E$13,"Diego")+COUNTIFS('S10'!$B$6:$B$13,$A40,'S10'!$E$6:$E$13,"Ambos")+COUNTIFS('Holgura'!$B$6:$B$11,$A40,'Holgura'!$E$6:$E$11,"Diego")+COUNTIFS('Holgura'!$B$6:$B$11,$A40,'Holgura'!$E$6:$E$11,"Ambos")+COUNTIFS('Entrega'!$B$6:$B$9,$A40,'Entrega'!$E$6:$E$9,"Diego")+COUNTIFS('Entrega'!$B$6:$B$9,$A40,'Entrega'!$E$6:$E$9,"Ambos")+COUNTIFS('Defensa'!$B$6:$B$10,$A40,'Defensa'!$E$6:$E$10,"Diego")+COUNTIFS('Defensa'!$B$6:$B$10,$A40,'Defensa'!$E$6:$E$10,"Ambos")</f>
         <v/>
       </c>
     </row>
@@ -9724,19 +9745,19 @@
         <v/>
       </c>
       <c r="D41" s="21">
-        <f>SUMIFS('S1'!$I$6:$I$32,'S1'!$B$6:$B$32,$A41,'S1'!$E$6:$E$32,"Víctor")+SUMIFS('S1'!$I$6:$I$32,'S1'!$B$6:$B$32,$A41,'S1'!$E$6:$E$32,"Ambos")+SUMIFS('S2'!$I$6:$I$23,'S2'!$B$6:$B$23,$A41,'S2'!$E$6:$E$23,"Víctor")+SUMIFS('S2'!$I$6:$I$23,'S2'!$B$6:$B$23,$A41,'S2'!$E$6:$E$23,"Ambos")+SUMIFS('S3'!$I$6:$I$19,'S3'!$B$6:$B$19,$A41,'S3'!$E$6:$E$19,"Víctor")+SUMIFS('S3'!$I$6:$I$19,'S3'!$B$6:$B$19,$A41,'S3'!$E$6:$E$19,"Ambos")+SUMIFS('S4'!$I$6:$I$20,'S4'!$B$6:$B$20,$A41,'S4'!$E$6:$E$20,"Víctor")+SUMIFS('S4'!$I$6:$I$20,'S4'!$B$6:$B$20,$A41,'S4'!$E$6:$E$20,"Ambos")+SUMIFS('S5'!$I$6:$I$20,'S5'!$B$6:$B$20,$A41,'S5'!$E$6:$E$20,"Víctor")+SUMIFS('S5'!$I$6:$I$20,'S5'!$B$6:$B$20,$A41,'S5'!$E$6:$E$20,"Ambos")+SUMIFS('S6'!$I$6:$I$17,'S6'!$B$6:$B$17,$A41,'S6'!$E$6:$E$17,"Víctor")+SUMIFS('S6'!$I$6:$I$17,'S6'!$B$6:$B$17,$A41,'S6'!$E$6:$E$17,"Ambos")+SUMIFS('S7'!$I$6:$I$19,'S7'!$B$6:$B$19,$A41,'S7'!$E$6:$E$19,"Víctor")+SUMIFS('S7'!$I$6:$I$19,'S7'!$B$6:$B$19,$A41,'S7'!$E$6:$E$19,"Ambos")+SUMIFS('S8'!$I$6:$I$23,'S8'!$B$6:$B$23,$A41,'S8'!$E$6:$E$23,"Víctor")+SUMIFS('S8'!$I$6:$I$23,'S8'!$B$6:$B$23,$A41,'S8'!$E$6:$E$23,"Ambos")+SUMIFS('S9'!$I$6:$I$15,'S9'!$B$6:$B$15,$A41,'S9'!$E$6:$E$15,"Víctor")+SUMIFS('S9'!$I$6:$I$15,'S9'!$B$6:$B$15,$A41,'S9'!$E$6:$E$15,"Ambos")+SUMIFS('S10'!$I$6:$I$13,'S10'!$B$6:$B$13,$A41,'S10'!$E$6:$E$13,"Víctor")+SUMIFS('S10'!$I$6:$I$13,'S10'!$B$6:$B$13,$A41,'S10'!$E$6:$E$13,"Ambos")+SUMIFS('Holgura'!$I$6:$I$11,'Holgura'!$B$6:$B$11,$A41,'Holgura'!$E$6:$E$11,"Víctor")+SUMIFS('Holgura'!$I$6:$I$11,'Holgura'!$B$6:$B$11,$A41,'Holgura'!$E$6:$E$11,"Ambos")+SUMIFS('Entrega'!$I$6:$I$9,'Entrega'!$B$6:$B$9,$A41,'Entrega'!$E$6:$E$9,"Víctor")+SUMIFS('Entrega'!$I$6:$I$9,'Entrega'!$B$6:$B$9,$A41,'Entrega'!$E$6:$E$9,"Ambos")+SUMIFS('Defensa'!$I$6:$I$10,'Defensa'!$B$6:$B$10,$A41,'Defensa'!$E$6:$E$10,"Víctor")+SUMIFS('Defensa'!$I$6:$I$10,'Defensa'!$B$6:$B$10,$A41,'Defensa'!$E$6:$E$10,"Ambos")</f>
+        <f>SUMIFS('S1'!$I$6:$I$32,'S1'!$B$6:$B$32,$A41,'S1'!$E$6:$E$32,"Víctor")+SUMIFS('S1'!$I$6:$I$32,'S1'!$B$6:$B$32,$A41,'S1'!$E$6:$E$32,"Ambos")+SUMIFS('S2'!$I$6:$I$23,'S2'!$B$6:$B$23,$A41,'S2'!$E$6:$E$23,"Víctor")+SUMIFS('S2'!$I$6:$I$23,'S2'!$B$6:$B$23,$A41,'S2'!$E$6:$E$23,"Ambos")+SUMIFS('S3'!$I$6:$I$24,'S3'!$B$6:$B$24,$A41,'S3'!$E$6:$E$24,"Víctor")+SUMIFS('S3'!$I$6:$I$24,'S3'!$B$6:$B$24,$A41,'S3'!$E$6:$E$24,"Ambos")+SUMIFS('S4'!$I$6:$I$22,'S4'!$B$6:$B$22,$A41,'S4'!$E$6:$E$22,"Víctor")+SUMIFS('S4'!$I$6:$I$22,'S4'!$B$6:$B$22,$A41,'S4'!$E$6:$E$22,"Ambos")+SUMIFS('S5'!$I$6:$I$20,'S5'!$B$6:$B$20,$A41,'S5'!$E$6:$E$20,"Víctor")+SUMIFS('S5'!$I$6:$I$20,'S5'!$B$6:$B$20,$A41,'S5'!$E$6:$E$20,"Ambos")+SUMIFS('S6'!$I$6:$I$17,'S6'!$B$6:$B$17,$A41,'S6'!$E$6:$E$17,"Víctor")+SUMIFS('S6'!$I$6:$I$17,'S6'!$B$6:$B$17,$A41,'S6'!$E$6:$E$17,"Ambos")+SUMIFS('S7'!$I$6:$I$19,'S7'!$B$6:$B$19,$A41,'S7'!$E$6:$E$19,"Víctor")+SUMIFS('S7'!$I$6:$I$19,'S7'!$B$6:$B$19,$A41,'S7'!$E$6:$E$19,"Ambos")+SUMIFS('S8'!$I$6:$I$23,'S8'!$B$6:$B$23,$A41,'S8'!$E$6:$E$23,"Víctor")+SUMIFS('S8'!$I$6:$I$23,'S8'!$B$6:$B$23,$A41,'S8'!$E$6:$E$23,"Ambos")+SUMIFS('S9'!$I$6:$I$15,'S9'!$B$6:$B$15,$A41,'S9'!$E$6:$E$15,"Víctor")+SUMIFS('S9'!$I$6:$I$15,'S9'!$B$6:$B$15,$A41,'S9'!$E$6:$E$15,"Ambos")+SUMIFS('S10'!$I$6:$I$13,'S10'!$B$6:$B$13,$A41,'S10'!$E$6:$E$13,"Víctor")+SUMIFS('S10'!$I$6:$I$13,'S10'!$B$6:$B$13,$A41,'S10'!$E$6:$E$13,"Ambos")+SUMIFS('Holgura'!$I$6:$I$11,'Holgura'!$B$6:$B$11,$A41,'Holgura'!$E$6:$E$11,"Víctor")+SUMIFS('Holgura'!$I$6:$I$11,'Holgura'!$B$6:$B$11,$A41,'Holgura'!$E$6:$E$11,"Ambos")+SUMIFS('Entrega'!$I$6:$I$9,'Entrega'!$B$6:$B$9,$A41,'Entrega'!$E$6:$E$9,"Víctor")+SUMIFS('Entrega'!$I$6:$I$9,'Entrega'!$B$6:$B$9,$A41,'Entrega'!$E$6:$E$9,"Ambos")+SUMIFS('Defensa'!$I$6:$I$10,'Defensa'!$B$6:$B$10,$A41,'Defensa'!$E$6:$E$10,"Víctor")+SUMIFS('Defensa'!$I$6:$I$10,'Defensa'!$B$6:$B$10,$A41,'Defensa'!$E$6:$E$10,"Ambos")</f>
         <v/>
       </c>
       <c r="E41" s="21">
-        <f>SUMIFS('S1'!$I$6:$I$32,'S1'!$B$6:$B$32,$A41,'S1'!$E$6:$E$32,"Diego")+SUMIFS('S1'!$I$6:$I$32,'S1'!$B$6:$B$32,$A41,'S1'!$E$6:$E$32,"Ambos")+SUMIFS('S2'!$I$6:$I$23,'S2'!$B$6:$B$23,$A41,'S2'!$E$6:$E$23,"Diego")+SUMIFS('S2'!$I$6:$I$23,'S2'!$B$6:$B$23,$A41,'S2'!$E$6:$E$23,"Ambos")+SUMIFS('S3'!$I$6:$I$19,'S3'!$B$6:$B$19,$A41,'S3'!$E$6:$E$19,"Diego")+SUMIFS('S3'!$I$6:$I$19,'S3'!$B$6:$B$19,$A41,'S3'!$E$6:$E$19,"Ambos")+SUMIFS('S4'!$I$6:$I$20,'S4'!$B$6:$B$20,$A41,'S4'!$E$6:$E$20,"Diego")+SUMIFS('S4'!$I$6:$I$20,'S4'!$B$6:$B$20,$A41,'S4'!$E$6:$E$20,"Ambos")+SUMIFS('S5'!$I$6:$I$20,'S5'!$B$6:$B$20,$A41,'S5'!$E$6:$E$20,"Diego")+SUMIFS('S5'!$I$6:$I$20,'S5'!$B$6:$B$20,$A41,'S5'!$E$6:$E$20,"Ambos")+SUMIFS('S6'!$I$6:$I$17,'S6'!$B$6:$B$17,$A41,'S6'!$E$6:$E$17,"Diego")+SUMIFS('S6'!$I$6:$I$17,'S6'!$B$6:$B$17,$A41,'S6'!$E$6:$E$17,"Ambos")+SUMIFS('S7'!$I$6:$I$19,'S7'!$B$6:$B$19,$A41,'S7'!$E$6:$E$19,"Diego")+SUMIFS('S7'!$I$6:$I$19,'S7'!$B$6:$B$19,$A41,'S7'!$E$6:$E$19,"Ambos")+SUMIFS('S8'!$I$6:$I$23,'S8'!$B$6:$B$23,$A41,'S8'!$E$6:$E$23,"Diego")+SUMIFS('S8'!$I$6:$I$23,'S8'!$B$6:$B$23,$A41,'S8'!$E$6:$E$23,"Ambos")+SUMIFS('S9'!$I$6:$I$15,'S9'!$B$6:$B$15,$A41,'S9'!$E$6:$E$15,"Diego")+SUMIFS('S9'!$I$6:$I$15,'S9'!$B$6:$B$15,$A41,'S9'!$E$6:$E$15,"Ambos")+SUMIFS('S10'!$I$6:$I$13,'S10'!$B$6:$B$13,$A41,'S10'!$E$6:$E$13,"Diego")+SUMIFS('S10'!$I$6:$I$13,'S10'!$B$6:$B$13,$A41,'S10'!$E$6:$E$13,"Ambos")+SUMIFS('Holgura'!$I$6:$I$11,'Holgura'!$B$6:$B$11,$A41,'Holgura'!$E$6:$E$11,"Diego")+SUMIFS('Holgura'!$I$6:$I$11,'Holgura'!$B$6:$B$11,$A41,'Holgura'!$E$6:$E$11,"Ambos")+SUMIFS('Entrega'!$I$6:$I$9,'Entrega'!$B$6:$B$9,$A41,'Entrega'!$E$6:$E$9,"Diego")+SUMIFS('Entrega'!$I$6:$I$9,'Entrega'!$B$6:$B$9,$A41,'Entrega'!$E$6:$E$9,"Ambos")+SUMIFS('Defensa'!$I$6:$I$10,'Defensa'!$B$6:$B$10,$A41,'Defensa'!$E$6:$E$10,"Diego")+SUMIFS('Defensa'!$I$6:$I$10,'Defensa'!$B$6:$B$10,$A41,'Defensa'!$E$6:$E$10,"Ambos")</f>
+        <f>SUMIFS('S1'!$I$6:$I$32,'S1'!$B$6:$B$32,$A41,'S1'!$E$6:$E$32,"Diego")+SUMIFS('S1'!$I$6:$I$32,'S1'!$B$6:$B$32,$A41,'S1'!$E$6:$E$32,"Ambos")+SUMIFS('S2'!$I$6:$I$23,'S2'!$B$6:$B$23,$A41,'S2'!$E$6:$E$23,"Diego")+SUMIFS('S2'!$I$6:$I$23,'S2'!$B$6:$B$23,$A41,'S2'!$E$6:$E$23,"Ambos")+SUMIFS('S3'!$I$6:$I$24,'S3'!$B$6:$B$24,$A41,'S3'!$E$6:$E$24,"Diego")+SUMIFS('S3'!$I$6:$I$24,'S3'!$B$6:$B$24,$A41,'S3'!$E$6:$E$24,"Ambos")+SUMIFS('S4'!$I$6:$I$22,'S4'!$B$6:$B$22,$A41,'S4'!$E$6:$E$22,"Diego")+SUMIFS('S4'!$I$6:$I$22,'S4'!$B$6:$B$22,$A41,'S4'!$E$6:$E$22,"Ambos")+SUMIFS('S5'!$I$6:$I$20,'S5'!$B$6:$B$20,$A41,'S5'!$E$6:$E$20,"Diego")+SUMIFS('S5'!$I$6:$I$20,'S5'!$B$6:$B$20,$A41,'S5'!$E$6:$E$20,"Ambos")+SUMIFS('S6'!$I$6:$I$17,'S6'!$B$6:$B$17,$A41,'S6'!$E$6:$E$17,"Diego")+SUMIFS('S6'!$I$6:$I$17,'S6'!$B$6:$B$17,$A41,'S6'!$E$6:$E$17,"Ambos")+SUMIFS('S7'!$I$6:$I$19,'S7'!$B$6:$B$19,$A41,'S7'!$E$6:$E$19,"Diego")+SUMIFS('S7'!$I$6:$I$19,'S7'!$B$6:$B$19,$A41,'S7'!$E$6:$E$19,"Ambos")+SUMIFS('S8'!$I$6:$I$23,'S8'!$B$6:$B$23,$A41,'S8'!$E$6:$E$23,"Diego")+SUMIFS('S8'!$I$6:$I$23,'S8'!$B$6:$B$23,$A41,'S8'!$E$6:$E$23,"Ambos")+SUMIFS('S9'!$I$6:$I$15,'S9'!$B$6:$B$15,$A41,'S9'!$E$6:$E$15,"Diego")+SUMIFS('S9'!$I$6:$I$15,'S9'!$B$6:$B$15,$A41,'S9'!$E$6:$E$15,"Ambos")+SUMIFS('S10'!$I$6:$I$13,'S10'!$B$6:$B$13,$A41,'S10'!$E$6:$E$13,"Diego")+SUMIFS('S10'!$I$6:$I$13,'S10'!$B$6:$B$13,$A41,'S10'!$E$6:$E$13,"Ambos")+SUMIFS('Holgura'!$I$6:$I$11,'Holgura'!$B$6:$B$11,$A41,'Holgura'!$E$6:$E$11,"Diego")+SUMIFS('Holgura'!$I$6:$I$11,'Holgura'!$B$6:$B$11,$A41,'Holgura'!$E$6:$E$11,"Ambos")+SUMIFS('Entrega'!$I$6:$I$9,'Entrega'!$B$6:$B$9,$A41,'Entrega'!$E$6:$E$9,"Diego")+SUMIFS('Entrega'!$I$6:$I$9,'Entrega'!$B$6:$B$9,$A41,'Entrega'!$E$6:$E$9,"Ambos")+SUMIFS('Defensa'!$I$6:$I$10,'Defensa'!$B$6:$B$10,$A41,'Defensa'!$E$6:$E$10,"Diego")+SUMIFS('Defensa'!$I$6:$I$10,'Defensa'!$B$6:$B$10,$A41,'Defensa'!$E$6:$E$10,"Ambos")</f>
         <v/>
       </c>
       <c r="F41" s="21">
-        <f>COUNTIFS('S1'!$B$6:$B$32,$A41,'S1'!$E$6:$E$32,"Víctor")+COUNTIFS('S1'!$B$6:$B$32,$A41,'S1'!$E$6:$E$32,"Ambos")+COUNTIFS('S2'!$B$6:$B$23,$A41,'S2'!$E$6:$E$23,"Víctor")+COUNTIFS('S2'!$B$6:$B$23,$A41,'S2'!$E$6:$E$23,"Ambos")+COUNTIFS('S3'!$B$6:$B$19,$A41,'S3'!$E$6:$E$19,"Víctor")+COUNTIFS('S3'!$B$6:$B$19,$A41,'S3'!$E$6:$E$19,"Ambos")+COUNTIFS('S4'!$B$6:$B$20,$A41,'S4'!$E$6:$E$20,"Víctor")+COUNTIFS('S4'!$B$6:$B$20,$A41,'S4'!$E$6:$E$20,"Ambos")+COUNTIFS('S5'!$B$6:$B$20,$A41,'S5'!$E$6:$E$20,"Víctor")+COUNTIFS('S5'!$B$6:$B$20,$A41,'S5'!$E$6:$E$20,"Ambos")+COUNTIFS('S6'!$B$6:$B$17,$A41,'S6'!$E$6:$E$17,"Víctor")+COUNTIFS('S6'!$B$6:$B$17,$A41,'S6'!$E$6:$E$17,"Ambos")+COUNTIFS('S7'!$B$6:$B$19,$A41,'S7'!$E$6:$E$19,"Víctor")+COUNTIFS('S7'!$B$6:$B$19,$A41,'S7'!$E$6:$E$19,"Ambos")+COUNTIFS('S8'!$B$6:$B$23,$A41,'S8'!$E$6:$E$23,"Víctor")+COUNTIFS('S8'!$B$6:$B$23,$A41,'S8'!$E$6:$E$23,"Ambos")+COUNTIFS('S9'!$B$6:$B$15,$A41,'S9'!$E$6:$E$15,"Víctor")+COUNTIFS('S9'!$B$6:$B$15,$A41,'S9'!$E$6:$E$15,"Ambos")+COUNTIFS('S10'!$B$6:$B$13,$A41,'S10'!$E$6:$E$13,"Víctor")+COUNTIFS('S10'!$B$6:$B$13,$A41,'S10'!$E$6:$E$13,"Ambos")+COUNTIFS('Holgura'!$B$6:$B$11,$A41,'Holgura'!$E$6:$E$11,"Víctor")+COUNTIFS('Holgura'!$B$6:$B$11,$A41,'Holgura'!$E$6:$E$11,"Ambos")+COUNTIFS('Entrega'!$B$6:$B$9,$A41,'Entrega'!$E$6:$E$9,"Víctor")+COUNTIFS('Entrega'!$B$6:$B$9,$A41,'Entrega'!$E$6:$E$9,"Ambos")+COUNTIFS('Defensa'!$B$6:$B$10,$A41,'Defensa'!$E$6:$E$10,"Víctor")+COUNTIFS('Defensa'!$B$6:$B$10,$A41,'Defensa'!$E$6:$E$10,"Ambos")</f>
+        <f>COUNTIFS('S1'!$B$6:$B$32,$A41,'S1'!$E$6:$E$32,"Víctor")+COUNTIFS('S1'!$B$6:$B$32,$A41,'S1'!$E$6:$E$32,"Ambos")+COUNTIFS('S2'!$B$6:$B$23,$A41,'S2'!$E$6:$E$23,"Víctor")+COUNTIFS('S2'!$B$6:$B$23,$A41,'S2'!$E$6:$E$23,"Ambos")+COUNTIFS('S3'!$B$6:$B$24,$A41,'S3'!$E$6:$E$24,"Víctor")+COUNTIFS('S3'!$B$6:$B$24,$A41,'S3'!$E$6:$E$24,"Ambos")+COUNTIFS('S4'!$B$6:$B$22,$A41,'S4'!$E$6:$E$22,"Víctor")+COUNTIFS('S4'!$B$6:$B$22,$A41,'S4'!$E$6:$E$22,"Ambos")+COUNTIFS('S5'!$B$6:$B$20,$A41,'S5'!$E$6:$E$20,"Víctor")+COUNTIFS('S5'!$B$6:$B$20,$A41,'S5'!$E$6:$E$20,"Ambos")+COUNTIFS('S6'!$B$6:$B$17,$A41,'S6'!$E$6:$E$17,"Víctor")+COUNTIFS('S6'!$B$6:$B$17,$A41,'S6'!$E$6:$E$17,"Ambos")+COUNTIFS('S7'!$B$6:$B$19,$A41,'S7'!$E$6:$E$19,"Víctor")+COUNTIFS('S7'!$B$6:$B$19,$A41,'S7'!$E$6:$E$19,"Ambos")+COUNTIFS('S8'!$B$6:$B$23,$A41,'S8'!$E$6:$E$23,"Víctor")+COUNTIFS('S8'!$B$6:$B$23,$A41,'S8'!$E$6:$E$23,"Ambos")+COUNTIFS('S9'!$B$6:$B$15,$A41,'S9'!$E$6:$E$15,"Víctor")+COUNTIFS('S9'!$B$6:$B$15,$A41,'S9'!$E$6:$E$15,"Ambos")+COUNTIFS('S10'!$B$6:$B$13,$A41,'S10'!$E$6:$E$13,"Víctor")+COUNTIFS('S10'!$B$6:$B$13,$A41,'S10'!$E$6:$E$13,"Ambos")+COUNTIFS('Holgura'!$B$6:$B$11,$A41,'Holgura'!$E$6:$E$11,"Víctor")+COUNTIFS('Holgura'!$B$6:$B$11,$A41,'Holgura'!$E$6:$E$11,"Ambos")+COUNTIFS('Entrega'!$B$6:$B$9,$A41,'Entrega'!$E$6:$E$9,"Víctor")+COUNTIFS('Entrega'!$B$6:$B$9,$A41,'Entrega'!$E$6:$E$9,"Ambos")+COUNTIFS('Defensa'!$B$6:$B$10,$A41,'Defensa'!$E$6:$E$10,"Víctor")+COUNTIFS('Defensa'!$B$6:$B$10,$A41,'Defensa'!$E$6:$E$10,"Ambos")</f>
         <v/>
       </c>
       <c r="G41" s="21">
-        <f>COUNTIFS('S1'!$B$6:$B$32,$A41,'S1'!$E$6:$E$32,"Diego")+COUNTIFS('S1'!$B$6:$B$32,$A41,'S1'!$E$6:$E$32,"Ambos")+COUNTIFS('S2'!$B$6:$B$23,$A41,'S2'!$E$6:$E$23,"Diego")+COUNTIFS('S2'!$B$6:$B$23,$A41,'S2'!$E$6:$E$23,"Ambos")+COUNTIFS('S3'!$B$6:$B$19,$A41,'S3'!$E$6:$E$19,"Diego")+COUNTIFS('S3'!$B$6:$B$19,$A41,'S3'!$E$6:$E$19,"Ambos")+COUNTIFS('S4'!$B$6:$B$20,$A41,'S4'!$E$6:$E$20,"Diego")+COUNTIFS('S4'!$B$6:$B$20,$A41,'S4'!$E$6:$E$20,"Ambos")+COUNTIFS('S5'!$B$6:$B$20,$A41,'S5'!$E$6:$E$20,"Diego")+COUNTIFS('S5'!$B$6:$B$20,$A41,'S5'!$E$6:$E$20,"Ambos")+COUNTIFS('S6'!$B$6:$B$17,$A41,'S6'!$E$6:$E$17,"Diego")+COUNTIFS('S6'!$B$6:$B$17,$A41,'S6'!$E$6:$E$17,"Ambos")+COUNTIFS('S7'!$B$6:$B$19,$A41,'S7'!$E$6:$E$19,"Diego")+COUNTIFS('S7'!$B$6:$B$19,$A41,'S7'!$E$6:$E$19,"Ambos")+COUNTIFS('S8'!$B$6:$B$23,$A41,'S8'!$E$6:$E$23,"Diego")+COUNTIFS('S8'!$B$6:$B$23,$A41,'S8'!$E$6:$E$23,"Ambos")+COUNTIFS('S9'!$B$6:$B$15,$A41,'S9'!$E$6:$E$15,"Diego")+COUNTIFS('S9'!$B$6:$B$15,$A41,'S9'!$E$6:$E$15,"Ambos")+COUNTIFS('S10'!$B$6:$B$13,$A41,'S10'!$E$6:$E$13,"Diego")+COUNTIFS('S10'!$B$6:$B$13,$A41,'S10'!$E$6:$E$13,"Ambos")+COUNTIFS('Holgura'!$B$6:$B$11,$A41,'Holgura'!$E$6:$E$11,"Diego")+COUNTIFS('Holgura'!$B$6:$B$11,$A41,'Holgura'!$E$6:$E$11,"Ambos")+COUNTIFS('Entrega'!$B$6:$B$9,$A41,'Entrega'!$E$6:$E$9,"Diego")+COUNTIFS('Entrega'!$B$6:$B$9,$A41,'Entrega'!$E$6:$E$9,"Ambos")+COUNTIFS('Defensa'!$B$6:$B$10,$A41,'Defensa'!$E$6:$E$10,"Diego")+COUNTIFS('Defensa'!$B$6:$B$10,$A41,'Defensa'!$E$6:$E$10,"Ambos")</f>
+        <f>COUNTIFS('S1'!$B$6:$B$32,$A41,'S1'!$E$6:$E$32,"Diego")+COUNTIFS('S1'!$B$6:$B$32,$A41,'S1'!$E$6:$E$32,"Ambos")+COUNTIFS('S2'!$B$6:$B$23,$A41,'S2'!$E$6:$E$23,"Diego")+COUNTIFS('S2'!$B$6:$B$23,$A41,'S2'!$E$6:$E$23,"Ambos")+COUNTIFS('S3'!$B$6:$B$24,$A41,'S3'!$E$6:$E$24,"Diego")+COUNTIFS('S3'!$B$6:$B$24,$A41,'S3'!$E$6:$E$24,"Ambos")+COUNTIFS('S4'!$B$6:$B$22,$A41,'S4'!$E$6:$E$22,"Diego")+COUNTIFS('S4'!$B$6:$B$22,$A41,'S4'!$E$6:$E$22,"Ambos")+COUNTIFS('S5'!$B$6:$B$20,$A41,'S5'!$E$6:$E$20,"Diego")+COUNTIFS('S5'!$B$6:$B$20,$A41,'S5'!$E$6:$E$20,"Ambos")+COUNTIFS('S6'!$B$6:$B$17,$A41,'S6'!$E$6:$E$17,"Diego")+COUNTIFS('S6'!$B$6:$B$17,$A41,'S6'!$E$6:$E$17,"Ambos")+COUNTIFS('S7'!$B$6:$B$19,$A41,'S7'!$E$6:$E$19,"Diego")+COUNTIFS('S7'!$B$6:$B$19,$A41,'S7'!$E$6:$E$19,"Ambos")+COUNTIFS('S8'!$B$6:$B$23,$A41,'S8'!$E$6:$E$23,"Diego")+COUNTIFS('S8'!$B$6:$B$23,$A41,'S8'!$E$6:$E$23,"Ambos")+COUNTIFS('S9'!$B$6:$B$15,$A41,'S9'!$E$6:$E$15,"Diego")+COUNTIFS('S9'!$B$6:$B$15,$A41,'S9'!$E$6:$E$15,"Ambos")+COUNTIFS('S10'!$B$6:$B$13,$A41,'S10'!$E$6:$E$13,"Diego")+COUNTIFS('S10'!$B$6:$B$13,$A41,'S10'!$E$6:$E$13,"Ambos")+COUNTIFS('Holgura'!$B$6:$B$11,$A41,'Holgura'!$E$6:$E$11,"Diego")+COUNTIFS('Holgura'!$B$6:$B$11,$A41,'Holgura'!$E$6:$E$11,"Ambos")+COUNTIFS('Entrega'!$B$6:$B$9,$A41,'Entrega'!$E$6:$E$9,"Diego")+COUNTIFS('Entrega'!$B$6:$B$9,$A41,'Entrega'!$E$6:$E$9,"Ambos")+COUNTIFS('Defensa'!$B$6:$B$10,$A41,'Defensa'!$E$6:$E$10,"Diego")+COUNTIFS('Defensa'!$B$6:$B$10,$A41,'Defensa'!$E$6:$E$10,"Ambos")</f>
         <v/>
       </c>
     </row>
@@ -9753,19 +9774,19 @@
         <v/>
       </c>
       <c r="D42" s="21">
-        <f>SUMIFS('S1'!$I$6:$I$32,'S1'!$B$6:$B$32,$A42,'S1'!$E$6:$E$32,"Víctor")+SUMIFS('S1'!$I$6:$I$32,'S1'!$B$6:$B$32,$A42,'S1'!$E$6:$E$32,"Ambos")+SUMIFS('S2'!$I$6:$I$23,'S2'!$B$6:$B$23,$A42,'S2'!$E$6:$E$23,"Víctor")+SUMIFS('S2'!$I$6:$I$23,'S2'!$B$6:$B$23,$A42,'S2'!$E$6:$E$23,"Ambos")+SUMIFS('S3'!$I$6:$I$19,'S3'!$B$6:$B$19,$A42,'S3'!$E$6:$E$19,"Víctor")+SUMIFS('S3'!$I$6:$I$19,'S3'!$B$6:$B$19,$A42,'S3'!$E$6:$E$19,"Ambos")+SUMIFS('S4'!$I$6:$I$20,'S4'!$B$6:$B$20,$A42,'S4'!$E$6:$E$20,"Víctor")+SUMIFS('S4'!$I$6:$I$20,'S4'!$B$6:$B$20,$A42,'S4'!$E$6:$E$20,"Ambos")+SUMIFS('S5'!$I$6:$I$20,'S5'!$B$6:$B$20,$A42,'S5'!$E$6:$E$20,"Víctor")+SUMIFS('S5'!$I$6:$I$20,'S5'!$B$6:$B$20,$A42,'S5'!$E$6:$E$20,"Ambos")+SUMIFS('S6'!$I$6:$I$17,'S6'!$B$6:$B$17,$A42,'S6'!$E$6:$E$17,"Víctor")+SUMIFS('S6'!$I$6:$I$17,'S6'!$B$6:$B$17,$A42,'S6'!$E$6:$E$17,"Ambos")+SUMIFS('S7'!$I$6:$I$19,'S7'!$B$6:$B$19,$A42,'S7'!$E$6:$E$19,"Víctor")+SUMIFS('S7'!$I$6:$I$19,'S7'!$B$6:$B$19,$A42,'S7'!$E$6:$E$19,"Ambos")+SUMIFS('S8'!$I$6:$I$23,'S8'!$B$6:$B$23,$A42,'S8'!$E$6:$E$23,"Víctor")+SUMIFS('S8'!$I$6:$I$23,'S8'!$B$6:$B$23,$A42,'S8'!$E$6:$E$23,"Ambos")+SUMIFS('S9'!$I$6:$I$15,'S9'!$B$6:$B$15,$A42,'S9'!$E$6:$E$15,"Víctor")+SUMIFS('S9'!$I$6:$I$15,'S9'!$B$6:$B$15,$A42,'S9'!$E$6:$E$15,"Ambos")+SUMIFS('S10'!$I$6:$I$13,'S10'!$B$6:$B$13,$A42,'S10'!$E$6:$E$13,"Víctor")+SUMIFS('S10'!$I$6:$I$13,'S10'!$B$6:$B$13,$A42,'S10'!$E$6:$E$13,"Ambos")+SUMIFS('Holgura'!$I$6:$I$11,'Holgura'!$B$6:$B$11,$A42,'Holgura'!$E$6:$E$11,"Víctor")+SUMIFS('Holgura'!$I$6:$I$11,'Holgura'!$B$6:$B$11,$A42,'Holgura'!$E$6:$E$11,"Ambos")+SUMIFS('Entrega'!$I$6:$I$9,'Entrega'!$B$6:$B$9,$A42,'Entrega'!$E$6:$E$9,"Víctor")+SUMIFS('Entrega'!$I$6:$I$9,'Entrega'!$B$6:$B$9,$A42,'Entrega'!$E$6:$E$9,"Ambos")+SUMIFS('Defensa'!$I$6:$I$10,'Defensa'!$B$6:$B$10,$A42,'Defensa'!$E$6:$E$10,"Víctor")+SUMIFS('Defensa'!$I$6:$I$10,'Defensa'!$B$6:$B$10,$A42,'Defensa'!$E$6:$E$10,"Ambos")</f>
+        <f>SUMIFS('S1'!$I$6:$I$32,'S1'!$B$6:$B$32,$A42,'S1'!$E$6:$E$32,"Víctor")+SUMIFS('S1'!$I$6:$I$32,'S1'!$B$6:$B$32,$A42,'S1'!$E$6:$E$32,"Ambos")+SUMIFS('S2'!$I$6:$I$23,'S2'!$B$6:$B$23,$A42,'S2'!$E$6:$E$23,"Víctor")+SUMIFS('S2'!$I$6:$I$23,'S2'!$B$6:$B$23,$A42,'S2'!$E$6:$E$23,"Ambos")+SUMIFS('S3'!$I$6:$I$24,'S3'!$B$6:$B$24,$A42,'S3'!$E$6:$E$24,"Víctor")+SUMIFS('S3'!$I$6:$I$24,'S3'!$B$6:$B$24,$A42,'S3'!$E$6:$E$24,"Ambos")+SUMIFS('S4'!$I$6:$I$22,'S4'!$B$6:$B$22,$A42,'S4'!$E$6:$E$22,"Víctor")+SUMIFS('S4'!$I$6:$I$22,'S4'!$B$6:$B$22,$A42,'S4'!$E$6:$E$22,"Ambos")+SUMIFS('S5'!$I$6:$I$20,'S5'!$B$6:$B$20,$A42,'S5'!$E$6:$E$20,"Víctor")+SUMIFS('S5'!$I$6:$I$20,'S5'!$B$6:$B$20,$A42,'S5'!$E$6:$E$20,"Ambos")+SUMIFS('S6'!$I$6:$I$17,'S6'!$B$6:$B$17,$A42,'S6'!$E$6:$E$17,"Víctor")+SUMIFS('S6'!$I$6:$I$17,'S6'!$B$6:$B$17,$A42,'S6'!$E$6:$E$17,"Ambos")+SUMIFS('S7'!$I$6:$I$19,'S7'!$B$6:$B$19,$A42,'S7'!$E$6:$E$19,"Víctor")+SUMIFS('S7'!$I$6:$I$19,'S7'!$B$6:$B$19,$A42,'S7'!$E$6:$E$19,"Ambos")+SUMIFS('S8'!$I$6:$I$23,'S8'!$B$6:$B$23,$A42,'S8'!$E$6:$E$23,"Víctor")+SUMIFS('S8'!$I$6:$I$23,'S8'!$B$6:$B$23,$A42,'S8'!$E$6:$E$23,"Ambos")+SUMIFS('S9'!$I$6:$I$15,'S9'!$B$6:$B$15,$A42,'S9'!$E$6:$E$15,"Víctor")+SUMIFS('S9'!$I$6:$I$15,'S9'!$B$6:$B$15,$A42,'S9'!$E$6:$E$15,"Ambos")+SUMIFS('S10'!$I$6:$I$13,'S10'!$B$6:$B$13,$A42,'S10'!$E$6:$E$13,"Víctor")+SUMIFS('S10'!$I$6:$I$13,'S10'!$B$6:$B$13,$A42,'S10'!$E$6:$E$13,"Ambos")+SUMIFS('Holgura'!$I$6:$I$11,'Holgura'!$B$6:$B$11,$A42,'Holgura'!$E$6:$E$11,"Víctor")+SUMIFS('Holgura'!$I$6:$I$11,'Holgura'!$B$6:$B$11,$A42,'Holgura'!$E$6:$E$11,"Ambos")+SUMIFS('Entrega'!$I$6:$I$9,'Entrega'!$B$6:$B$9,$A42,'Entrega'!$E$6:$E$9,"Víctor")+SUMIFS('Entrega'!$I$6:$I$9,'Entrega'!$B$6:$B$9,$A42,'Entrega'!$E$6:$E$9,"Ambos")+SUMIFS('Defensa'!$I$6:$I$10,'Defensa'!$B$6:$B$10,$A42,'Defensa'!$E$6:$E$10,"Víctor")+SUMIFS('Defensa'!$I$6:$I$10,'Defensa'!$B$6:$B$10,$A42,'Defensa'!$E$6:$E$10,"Ambos")</f>
         <v/>
       </c>
       <c r="E42" s="21">
-        <f>SUMIFS('S1'!$I$6:$I$32,'S1'!$B$6:$B$32,$A42,'S1'!$E$6:$E$32,"Diego")+SUMIFS('S1'!$I$6:$I$32,'S1'!$B$6:$B$32,$A42,'S1'!$E$6:$E$32,"Ambos")+SUMIFS('S2'!$I$6:$I$23,'S2'!$B$6:$B$23,$A42,'S2'!$E$6:$E$23,"Diego")+SUMIFS('S2'!$I$6:$I$23,'S2'!$B$6:$B$23,$A42,'S2'!$E$6:$E$23,"Ambos")+SUMIFS('S3'!$I$6:$I$19,'S3'!$B$6:$B$19,$A42,'S3'!$E$6:$E$19,"Diego")+SUMIFS('S3'!$I$6:$I$19,'S3'!$B$6:$B$19,$A42,'S3'!$E$6:$E$19,"Ambos")+SUMIFS('S4'!$I$6:$I$20,'S4'!$B$6:$B$20,$A42,'S4'!$E$6:$E$20,"Diego")+SUMIFS('S4'!$I$6:$I$20,'S4'!$B$6:$B$20,$A42,'S4'!$E$6:$E$20,"Ambos")+SUMIFS('S5'!$I$6:$I$20,'S5'!$B$6:$B$20,$A42,'S5'!$E$6:$E$20,"Diego")+SUMIFS('S5'!$I$6:$I$20,'S5'!$B$6:$B$20,$A42,'S5'!$E$6:$E$20,"Ambos")+SUMIFS('S6'!$I$6:$I$17,'S6'!$B$6:$B$17,$A42,'S6'!$E$6:$E$17,"Diego")+SUMIFS('S6'!$I$6:$I$17,'S6'!$B$6:$B$17,$A42,'S6'!$E$6:$E$17,"Ambos")+SUMIFS('S7'!$I$6:$I$19,'S7'!$B$6:$B$19,$A42,'S7'!$E$6:$E$19,"Diego")+SUMIFS('S7'!$I$6:$I$19,'S7'!$B$6:$B$19,$A42,'S7'!$E$6:$E$19,"Ambos")+SUMIFS('S8'!$I$6:$I$23,'S8'!$B$6:$B$23,$A42,'S8'!$E$6:$E$23,"Diego")+SUMIFS('S8'!$I$6:$I$23,'S8'!$B$6:$B$23,$A42,'S8'!$E$6:$E$23,"Ambos")+SUMIFS('S9'!$I$6:$I$15,'S9'!$B$6:$B$15,$A42,'S9'!$E$6:$E$15,"Diego")+SUMIFS('S9'!$I$6:$I$15,'S9'!$B$6:$B$15,$A42,'S9'!$E$6:$E$15,"Ambos")+SUMIFS('S10'!$I$6:$I$13,'S10'!$B$6:$B$13,$A42,'S10'!$E$6:$E$13,"Diego")+SUMIFS('S10'!$I$6:$I$13,'S10'!$B$6:$B$13,$A42,'S10'!$E$6:$E$13,"Ambos")+SUMIFS('Holgura'!$I$6:$I$11,'Holgura'!$B$6:$B$11,$A42,'Holgura'!$E$6:$E$11,"Diego")+SUMIFS('Holgura'!$I$6:$I$11,'Holgura'!$B$6:$B$11,$A42,'Holgura'!$E$6:$E$11,"Ambos")+SUMIFS('Entrega'!$I$6:$I$9,'Entrega'!$B$6:$B$9,$A42,'Entrega'!$E$6:$E$9,"Diego")+SUMIFS('Entrega'!$I$6:$I$9,'Entrega'!$B$6:$B$9,$A42,'Entrega'!$E$6:$E$9,"Ambos")+SUMIFS('Defensa'!$I$6:$I$10,'Defensa'!$B$6:$B$10,$A42,'Defensa'!$E$6:$E$10,"Diego")+SUMIFS('Defensa'!$I$6:$I$10,'Defensa'!$B$6:$B$10,$A42,'Defensa'!$E$6:$E$10,"Ambos")</f>
+        <f>SUMIFS('S1'!$I$6:$I$32,'S1'!$B$6:$B$32,$A42,'S1'!$E$6:$E$32,"Diego")+SUMIFS('S1'!$I$6:$I$32,'S1'!$B$6:$B$32,$A42,'S1'!$E$6:$E$32,"Ambos")+SUMIFS('S2'!$I$6:$I$23,'S2'!$B$6:$B$23,$A42,'S2'!$E$6:$E$23,"Diego")+SUMIFS('S2'!$I$6:$I$23,'S2'!$B$6:$B$23,$A42,'S2'!$E$6:$E$23,"Ambos")+SUMIFS('S3'!$I$6:$I$24,'S3'!$B$6:$B$24,$A42,'S3'!$E$6:$E$24,"Diego")+SUMIFS('S3'!$I$6:$I$24,'S3'!$B$6:$B$24,$A42,'S3'!$E$6:$E$24,"Ambos")+SUMIFS('S4'!$I$6:$I$22,'S4'!$B$6:$B$22,$A42,'S4'!$E$6:$E$22,"Diego")+SUMIFS('S4'!$I$6:$I$22,'S4'!$B$6:$B$22,$A42,'S4'!$E$6:$E$22,"Ambos")+SUMIFS('S5'!$I$6:$I$20,'S5'!$B$6:$B$20,$A42,'S5'!$E$6:$E$20,"Diego")+SUMIFS('S5'!$I$6:$I$20,'S5'!$B$6:$B$20,$A42,'S5'!$E$6:$E$20,"Ambos")+SUMIFS('S6'!$I$6:$I$17,'S6'!$B$6:$B$17,$A42,'S6'!$E$6:$E$17,"Diego")+SUMIFS('S6'!$I$6:$I$17,'S6'!$B$6:$B$17,$A42,'S6'!$E$6:$E$17,"Ambos")+SUMIFS('S7'!$I$6:$I$19,'S7'!$B$6:$B$19,$A42,'S7'!$E$6:$E$19,"Diego")+SUMIFS('S7'!$I$6:$I$19,'S7'!$B$6:$B$19,$A42,'S7'!$E$6:$E$19,"Ambos")+SUMIFS('S8'!$I$6:$I$23,'S8'!$B$6:$B$23,$A42,'S8'!$E$6:$E$23,"Diego")+SUMIFS('S8'!$I$6:$I$23,'S8'!$B$6:$B$23,$A42,'S8'!$E$6:$E$23,"Ambos")+SUMIFS('S9'!$I$6:$I$15,'S9'!$B$6:$B$15,$A42,'S9'!$E$6:$E$15,"Diego")+SUMIFS('S9'!$I$6:$I$15,'S9'!$B$6:$B$15,$A42,'S9'!$E$6:$E$15,"Ambos")+SUMIFS('S10'!$I$6:$I$13,'S10'!$B$6:$B$13,$A42,'S10'!$E$6:$E$13,"Diego")+SUMIFS('S10'!$I$6:$I$13,'S10'!$B$6:$B$13,$A42,'S10'!$E$6:$E$13,"Ambos")+SUMIFS('Holgura'!$I$6:$I$11,'Holgura'!$B$6:$B$11,$A42,'Holgura'!$E$6:$E$11,"Diego")+SUMIFS('Holgura'!$I$6:$I$11,'Holgura'!$B$6:$B$11,$A42,'Holgura'!$E$6:$E$11,"Ambos")+SUMIFS('Entrega'!$I$6:$I$9,'Entrega'!$B$6:$B$9,$A42,'Entrega'!$E$6:$E$9,"Diego")+SUMIFS('Entrega'!$I$6:$I$9,'Entrega'!$B$6:$B$9,$A42,'Entrega'!$E$6:$E$9,"Ambos")+SUMIFS('Defensa'!$I$6:$I$10,'Defensa'!$B$6:$B$10,$A42,'Defensa'!$E$6:$E$10,"Diego")+SUMIFS('Defensa'!$I$6:$I$10,'Defensa'!$B$6:$B$10,$A42,'Defensa'!$E$6:$E$10,"Ambos")</f>
         <v/>
       </c>
       <c r="F42" s="21">
-        <f>COUNTIFS('S1'!$B$6:$B$32,$A42,'S1'!$E$6:$E$32,"Víctor")+COUNTIFS('S1'!$B$6:$B$32,$A42,'S1'!$E$6:$E$32,"Ambos")+COUNTIFS('S2'!$B$6:$B$23,$A42,'S2'!$E$6:$E$23,"Víctor")+COUNTIFS('S2'!$B$6:$B$23,$A42,'S2'!$E$6:$E$23,"Ambos")+COUNTIFS('S3'!$B$6:$B$19,$A42,'S3'!$E$6:$E$19,"Víctor")+COUNTIFS('S3'!$B$6:$B$19,$A42,'S3'!$E$6:$E$19,"Ambos")+COUNTIFS('S4'!$B$6:$B$20,$A42,'S4'!$E$6:$E$20,"Víctor")+COUNTIFS('S4'!$B$6:$B$20,$A42,'S4'!$E$6:$E$20,"Ambos")+COUNTIFS('S5'!$B$6:$B$20,$A42,'S5'!$E$6:$E$20,"Víctor")+COUNTIFS('S5'!$B$6:$B$20,$A42,'S5'!$E$6:$E$20,"Ambos")+COUNTIFS('S6'!$B$6:$B$17,$A42,'S6'!$E$6:$E$17,"Víctor")+COUNTIFS('S6'!$B$6:$B$17,$A42,'S6'!$E$6:$E$17,"Ambos")+COUNTIFS('S7'!$B$6:$B$19,$A42,'S7'!$E$6:$E$19,"Víctor")+COUNTIFS('S7'!$B$6:$B$19,$A42,'S7'!$E$6:$E$19,"Ambos")+COUNTIFS('S8'!$B$6:$B$23,$A42,'S8'!$E$6:$E$23,"Víctor")+COUNTIFS('S8'!$B$6:$B$23,$A42,'S8'!$E$6:$E$23,"Ambos")+COUNTIFS('S9'!$B$6:$B$15,$A42,'S9'!$E$6:$E$15,"Víctor")+COUNTIFS('S9'!$B$6:$B$15,$A42,'S9'!$E$6:$E$15,"Ambos")+COUNTIFS('S10'!$B$6:$B$13,$A42,'S10'!$E$6:$E$13,"Víctor")+COUNTIFS('S10'!$B$6:$B$13,$A42,'S10'!$E$6:$E$13,"Ambos")+COUNTIFS('Holgura'!$B$6:$B$11,$A42,'Holgura'!$E$6:$E$11,"Víctor")+COUNTIFS('Holgura'!$B$6:$B$11,$A42,'Holgura'!$E$6:$E$11,"Ambos")+COUNTIFS('Entrega'!$B$6:$B$9,$A42,'Entrega'!$E$6:$E$9,"Víctor")+COUNTIFS('Entrega'!$B$6:$B$9,$A42,'Entrega'!$E$6:$E$9,"Ambos")+COUNTIFS('Defensa'!$B$6:$B$10,$A42,'Defensa'!$E$6:$E$10,"Víctor")+COUNTIFS('Defensa'!$B$6:$B$10,$A42,'Defensa'!$E$6:$E$10,"Ambos")</f>
+        <f>COUNTIFS('S1'!$B$6:$B$32,$A42,'S1'!$E$6:$E$32,"Víctor")+COUNTIFS('S1'!$B$6:$B$32,$A42,'S1'!$E$6:$E$32,"Ambos")+COUNTIFS('S2'!$B$6:$B$23,$A42,'S2'!$E$6:$E$23,"Víctor")+COUNTIFS('S2'!$B$6:$B$23,$A42,'S2'!$E$6:$E$23,"Ambos")+COUNTIFS('S3'!$B$6:$B$24,$A42,'S3'!$E$6:$E$24,"Víctor")+COUNTIFS('S3'!$B$6:$B$24,$A42,'S3'!$E$6:$E$24,"Ambos")+COUNTIFS('S4'!$B$6:$B$22,$A42,'S4'!$E$6:$E$22,"Víctor")+COUNTIFS('S4'!$B$6:$B$22,$A42,'S4'!$E$6:$E$22,"Ambos")+COUNTIFS('S5'!$B$6:$B$20,$A42,'S5'!$E$6:$E$20,"Víctor")+COUNTIFS('S5'!$B$6:$B$20,$A42,'S5'!$E$6:$E$20,"Ambos")+COUNTIFS('S6'!$B$6:$B$17,$A42,'S6'!$E$6:$E$17,"Víctor")+COUNTIFS('S6'!$B$6:$B$17,$A42,'S6'!$E$6:$E$17,"Ambos")+COUNTIFS('S7'!$B$6:$B$19,$A42,'S7'!$E$6:$E$19,"Víctor")+COUNTIFS('S7'!$B$6:$B$19,$A42,'S7'!$E$6:$E$19,"Ambos")+COUNTIFS('S8'!$B$6:$B$23,$A42,'S8'!$E$6:$E$23,"Víctor")+COUNTIFS('S8'!$B$6:$B$23,$A42,'S8'!$E$6:$E$23,"Ambos")+COUNTIFS('S9'!$B$6:$B$15,$A42,'S9'!$E$6:$E$15,"Víctor")+COUNTIFS('S9'!$B$6:$B$15,$A42,'S9'!$E$6:$E$15,"Ambos")+COUNTIFS('S10'!$B$6:$B$13,$A42,'S10'!$E$6:$E$13,"Víctor")+COUNTIFS('S10'!$B$6:$B$13,$A42,'S10'!$E$6:$E$13,"Ambos")+COUNTIFS('Holgura'!$B$6:$B$11,$A42,'Holgura'!$E$6:$E$11,"Víctor")+COUNTIFS('Holgura'!$B$6:$B$11,$A42,'Holgura'!$E$6:$E$11,"Ambos")+COUNTIFS('Entrega'!$B$6:$B$9,$A42,'Entrega'!$E$6:$E$9,"Víctor")+COUNTIFS('Entrega'!$B$6:$B$9,$A42,'Entrega'!$E$6:$E$9,"Ambos")+COUNTIFS('Defensa'!$B$6:$B$10,$A42,'Defensa'!$E$6:$E$10,"Víctor")+COUNTIFS('Defensa'!$B$6:$B$10,$A42,'Defensa'!$E$6:$E$10,"Ambos")</f>
         <v/>
       </c>
       <c r="G42" s="21">
-        <f>COUNTIFS('S1'!$B$6:$B$32,$A42,'S1'!$E$6:$E$32,"Diego")+COUNTIFS('S1'!$B$6:$B$32,$A42,'S1'!$E$6:$E$32,"Ambos")+COUNTIFS('S2'!$B$6:$B$23,$A42,'S2'!$E$6:$E$23,"Diego")+COUNTIFS('S2'!$B$6:$B$23,$A42,'S2'!$E$6:$E$23,"Ambos")+COUNTIFS('S3'!$B$6:$B$19,$A42,'S3'!$E$6:$E$19,"Diego")+COUNTIFS('S3'!$B$6:$B$19,$A42,'S3'!$E$6:$E$19,"Ambos")+COUNTIFS('S4'!$B$6:$B$20,$A42,'S4'!$E$6:$E$20,"Diego")+COUNTIFS('S4'!$B$6:$B$20,$A42,'S4'!$E$6:$E$20,"Ambos")+COUNTIFS('S5'!$B$6:$B$20,$A42,'S5'!$E$6:$E$20,"Diego")+COUNTIFS('S5'!$B$6:$B$20,$A42,'S5'!$E$6:$E$20,"Ambos")+COUNTIFS('S6'!$B$6:$B$17,$A42,'S6'!$E$6:$E$17,"Diego")+COUNTIFS('S6'!$B$6:$B$17,$A42,'S6'!$E$6:$E$17,"Ambos")+COUNTIFS('S7'!$B$6:$B$19,$A42,'S7'!$E$6:$E$19,"Diego")+COUNTIFS('S7'!$B$6:$B$19,$A42,'S7'!$E$6:$E$19,"Ambos")+COUNTIFS('S8'!$B$6:$B$23,$A42,'S8'!$E$6:$E$23,"Diego")+COUNTIFS('S8'!$B$6:$B$23,$A42,'S8'!$E$6:$E$23,"Ambos")+COUNTIFS('S9'!$B$6:$B$15,$A42,'S9'!$E$6:$E$15,"Diego")+COUNTIFS('S9'!$B$6:$B$15,$A42,'S9'!$E$6:$E$15,"Ambos")+COUNTIFS('S10'!$B$6:$B$13,$A42,'S10'!$E$6:$E$13,"Diego")+COUNTIFS('S10'!$B$6:$B$13,$A42,'S10'!$E$6:$E$13,"Ambos")+COUNTIFS('Holgura'!$B$6:$B$11,$A42,'Holgura'!$E$6:$E$11,"Diego")+COUNTIFS('Holgura'!$B$6:$B$11,$A42,'Holgura'!$E$6:$E$11,"Ambos")+COUNTIFS('Entrega'!$B$6:$B$9,$A42,'Entrega'!$E$6:$E$9,"Diego")+COUNTIFS('Entrega'!$B$6:$B$9,$A42,'Entrega'!$E$6:$E$9,"Ambos")+COUNTIFS('Defensa'!$B$6:$B$10,$A42,'Defensa'!$E$6:$E$10,"Diego")+COUNTIFS('Defensa'!$B$6:$B$10,$A42,'Defensa'!$E$6:$E$10,"Ambos")</f>
+        <f>COUNTIFS('S1'!$B$6:$B$32,$A42,'S1'!$E$6:$E$32,"Diego")+COUNTIFS('S1'!$B$6:$B$32,$A42,'S1'!$E$6:$E$32,"Ambos")+COUNTIFS('S2'!$B$6:$B$23,$A42,'S2'!$E$6:$E$23,"Diego")+COUNTIFS('S2'!$B$6:$B$23,$A42,'S2'!$E$6:$E$23,"Ambos")+COUNTIFS('S3'!$B$6:$B$24,$A42,'S3'!$E$6:$E$24,"Diego")+COUNTIFS('S3'!$B$6:$B$24,$A42,'S3'!$E$6:$E$24,"Ambos")+COUNTIFS('S4'!$B$6:$B$22,$A42,'S4'!$E$6:$E$22,"Diego")+COUNTIFS('S4'!$B$6:$B$22,$A42,'S4'!$E$6:$E$22,"Ambos")+COUNTIFS('S5'!$B$6:$B$20,$A42,'S5'!$E$6:$E$20,"Diego")+COUNTIFS('S5'!$B$6:$B$20,$A42,'S5'!$E$6:$E$20,"Ambos")+COUNTIFS('S6'!$B$6:$B$17,$A42,'S6'!$E$6:$E$17,"Diego")+COUNTIFS('S6'!$B$6:$B$17,$A42,'S6'!$E$6:$E$17,"Ambos")+COUNTIFS('S7'!$B$6:$B$19,$A42,'S7'!$E$6:$E$19,"Diego")+COUNTIFS('S7'!$B$6:$B$19,$A42,'S7'!$E$6:$E$19,"Ambos")+COUNTIFS('S8'!$B$6:$B$23,$A42,'S8'!$E$6:$E$23,"Diego")+COUNTIFS('S8'!$B$6:$B$23,$A42,'S8'!$E$6:$E$23,"Ambos")+COUNTIFS('S9'!$B$6:$B$15,$A42,'S9'!$E$6:$E$15,"Diego")+COUNTIFS('S9'!$B$6:$B$15,$A42,'S9'!$E$6:$E$15,"Ambos")+COUNTIFS('S10'!$B$6:$B$13,$A42,'S10'!$E$6:$E$13,"Diego")+COUNTIFS('S10'!$B$6:$B$13,$A42,'S10'!$E$6:$E$13,"Ambos")+COUNTIFS('Holgura'!$B$6:$B$11,$A42,'Holgura'!$E$6:$E$11,"Diego")+COUNTIFS('Holgura'!$B$6:$B$11,$A42,'Holgura'!$E$6:$E$11,"Ambos")+COUNTIFS('Entrega'!$B$6:$B$9,$A42,'Entrega'!$E$6:$E$9,"Diego")+COUNTIFS('Entrega'!$B$6:$B$9,$A42,'Entrega'!$E$6:$E$9,"Ambos")+COUNTIFS('Defensa'!$B$6:$B$10,$A42,'Defensa'!$E$6:$E$10,"Diego")+COUNTIFS('Defensa'!$B$6:$B$10,$A42,'Defensa'!$E$6:$E$10,"Ambos")</f>
         <v/>
       </c>
     </row>
@@ -9782,19 +9803,19 @@
         <v/>
       </c>
       <c r="D43" s="21">
-        <f>SUMIFS('S1'!$I$6:$I$32,'S1'!$B$6:$B$32,$A43,'S1'!$E$6:$E$32,"Víctor")+SUMIFS('S1'!$I$6:$I$32,'S1'!$B$6:$B$32,$A43,'S1'!$E$6:$E$32,"Ambos")+SUMIFS('S2'!$I$6:$I$23,'S2'!$B$6:$B$23,$A43,'S2'!$E$6:$E$23,"Víctor")+SUMIFS('S2'!$I$6:$I$23,'S2'!$B$6:$B$23,$A43,'S2'!$E$6:$E$23,"Ambos")+SUMIFS('S3'!$I$6:$I$19,'S3'!$B$6:$B$19,$A43,'S3'!$E$6:$E$19,"Víctor")+SUMIFS('S3'!$I$6:$I$19,'S3'!$B$6:$B$19,$A43,'S3'!$E$6:$E$19,"Ambos")+SUMIFS('S4'!$I$6:$I$20,'S4'!$B$6:$B$20,$A43,'S4'!$E$6:$E$20,"Víctor")+SUMIFS('S4'!$I$6:$I$20,'S4'!$B$6:$B$20,$A43,'S4'!$E$6:$E$20,"Ambos")+SUMIFS('S5'!$I$6:$I$20,'S5'!$B$6:$B$20,$A43,'S5'!$E$6:$E$20,"Víctor")+SUMIFS('S5'!$I$6:$I$20,'S5'!$B$6:$B$20,$A43,'S5'!$E$6:$E$20,"Ambos")+SUMIFS('S6'!$I$6:$I$17,'S6'!$B$6:$B$17,$A43,'S6'!$E$6:$E$17,"Víctor")+SUMIFS('S6'!$I$6:$I$17,'S6'!$B$6:$B$17,$A43,'S6'!$E$6:$E$17,"Ambos")+SUMIFS('S7'!$I$6:$I$19,'S7'!$B$6:$B$19,$A43,'S7'!$E$6:$E$19,"Víctor")+SUMIFS('S7'!$I$6:$I$19,'S7'!$B$6:$B$19,$A43,'S7'!$E$6:$E$19,"Ambos")+SUMIFS('S8'!$I$6:$I$23,'S8'!$B$6:$B$23,$A43,'S8'!$E$6:$E$23,"Víctor")+SUMIFS('S8'!$I$6:$I$23,'S8'!$B$6:$B$23,$A43,'S8'!$E$6:$E$23,"Ambos")+SUMIFS('S9'!$I$6:$I$15,'S9'!$B$6:$B$15,$A43,'S9'!$E$6:$E$15,"Víctor")+SUMIFS('S9'!$I$6:$I$15,'S9'!$B$6:$B$15,$A43,'S9'!$E$6:$E$15,"Ambos")+SUMIFS('S10'!$I$6:$I$13,'S10'!$B$6:$B$13,$A43,'S10'!$E$6:$E$13,"Víctor")+SUMIFS('S10'!$I$6:$I$13,'S10'!$B$6:$B$13,$A43,'S10'!$E$6:$E$13,"Ambos")+SUMIFS('Holgura'!$I$6:$I$11,'Holgura'!$B$6:$B$11,$A43,'Holgura'!$E$6:$E$11,"Víctor")+SUMIFS('Holgura'!$I$6:$I$11,'Holgura'!$B$6:$B$11,$A43,'Holgura'!$E$6:$E$11,"Ambos")+SUMIFS('Entrega'!$I$6:$I$9,'Entrega'!$B$6:$B$9,$A43,'Entrega'!$E$6:$E$9,"Víctor")+SUMIFS('Entrega'!$I$6:$I$9,'Entrega'!$B$6:$B$9,$A43,'Entrega'!$E$6:$E$9,"Ambos")+SUMIFS('Defensa'!$I$6:$I$10,'Defensa'!$B$6:$B$10,$A43,'Defensa'!$E$6:$E$10,"Víctor")+SUMIFS('Defensa'!$I$6:$I$10,'Defensa'!$B$6:$B$10,$A43,'Defensa'!$E$6:$E$10,"Ambos")</f>
+        <f>SUMIFS('S1'!$I$6:$I$32,'S1'!$B$6:$B$32,$A43,'S1'!$E$6:$E$32,"Víctor")+SUMIFS('S1'!$I$6:$I$32,'S1'!$B$6:$B$32,$A43,'S1'!$E$6:$E$32,"Ambos")+SUMIFS('S2'!$I$6:$I$23,'S2'!$B$6:$B$23,$A43,'S2'!$E$6:$E$23,"Víctor")+SUMIFS('S2'!$I$6:$I$23,'S2'!$B$6:$B$23,$A43,'S2'!$E$6:$E$23,"Ambos")+SUMIFS('S3'!$I$6:$I$24,'S3'!$B$6:$B$24,$A43,'S3'!$E$6:$E$24,"Víctor")+SUMIFS('S3'!$I$6:$I$24,'S3'!$B$6:$B$24,$A43,'S3'!$E$6:$E$24,"Ambos")+SUMIFS('S4'!$I$6:$I$22,'S4'!$B$6:$B$22,$A43,'S4'!$E$6:$E$22,"Víctor")+SUMIFS('S4'!$I$6:$I$22,'S4'!$B$6:$B$22,$A43,'S4'!$E$6:$E$22,"Ambos")+SUMIFS('S5'!$I$6:$I$20,'S5'!$B$6:$B$20,$A43,'S5'!$E$6:$E$20,"Víctor")+SUMIFS('S5'!$I$6:$I$20,'S5'!$B$6:$B$20,$A43,'S5'!$E$6:$E$20,"Ambos")+SUMIFS('S6'!$I$6:$I$17,'S6'!$B$6:$B$17,$A43,'S6'!$E$6:$E$17,"Víctor")+SUMIFS('S6'!$I$6:$I$17,'S6'!$B$6:$B$17,$A43,'S6'!$E$6:$E$17,"Ambos")+SUMIFS('S7'!$I$6:$I$19,'S7'!$B$6:$B$19,$A43,'S7'!$E$6:$E$19,"Víctor")+SUMIFS('S7'!$I$6:$I$19,'S7'!$B$6:$B$19,$A43,'S7'!$E$6:$E$19,"Ambos")+SUMIFS('S8'!$I$6:$I$23,'S8'!$B$6:$B$23,$A43,'S8'!$E$6:$E$23,"Víctor")+SUMIFS('S8'!$I$6:$I$23,'S8'!$B$6:$B$23,$A43,'S8'!$E$6:$E$23,"Ambos")+SUMIFS('S9'!$I$6:$I$15,'S9'!$B$6:$B$15,$A43,'S9'!$E$6:$E$15,"Víctor")+SUMIFS('S9'!$I$6:$I$15,'S9'!$B$6:$B$15,$A43,'S9'!$E$6:$E$15,"Ambos")+SUMIFS('S10'!$I$6:$I$13,'S10'!$B$6:$B$13,$A43,'S10'!$E$6:$E$13,"Víctor")+SUMIFS('S10'!$I$6:$I$13,'S10'!$B$6:$B$13,$A43,'S10'!$E$6:$E$13,"Ambos")+SUMIFS('Holgura'!$I$6:$I$11,'Holgura'!$B$6:$B$11,$A43,'Holgura'!$E$6:$E$11,"Víctor")+SUMIFS('Holgura'!$I$6:$I$11,'Holgura'!$B$6:$B$11,$A43,'Holgura'!$E$6:$E$11,"Ambos")+SUMIFS('Entrega'!$I$6:$I$9,'Entrega'!$B$6:$B$9,$A43,'Entrega'!$E$6:$E$9,"Víctor")+SUMIFS('Entrega'!$I$6:$I$9,'Entrega'!$B$6:$B$9,$A43,'Entrega'!$E$6:$E$9,"Ambos")+SUMIFS('Defensa'!$I$6:$I$10,'Defensa'!$B$6:$B$10,$A43,'Defensa'!$E$6:$E$10,"Víctor")+SUMIFS('Defensa'!$I$6:$I$10,'Defensa'!$B$6:$B$10,$A43,'Defensa'!$E$6:$E$10,"Ambos")</f>
         <v/>
       </c>
       <c r="E43" s="21">
-        <f>SUMIFS('S1'!$I$6:$I$32,'S1'!$B$6:$B$32,$A43,'S1'!$E$6:$E$32,"Diego")+SUMIFS('S1'!$I$6:$I$32,'S1'!$B$6:$B$32,$A43,'S1'!$E$6:$E$32,"Ambos")+SUMIFS('S2'!$I$6:$I$23,'S2'!$B$6:$B$23,$A43,'S2'!$E$6:$E$23,"Diego")+SUMIFS('S2'!$I$6:$I$23,'S2'!$B$6:$B$23,$A43,'S2'!$E$6:$E$23,"Ambos")+SUMIFS('S3'!$I$6:$I$19,'S3'!$B$6:$B$19,$A43,'S3'!$E$6:$E$19,"Diego")+SUMIFS('S3'!$I$6:$I$19,'S3'!$B$6:$B$19,$A43,'S3'!$E$6:$E$19,"Ambos")+SUMIFS('S4'!$I$6:$I$20,'S4'!$B$6:$B$20,$A43,'S4'!$E$6:$E$20,"Diego")+SUMIFS('S4'!$I$6:$I$20,'S4'!$B$6:$B$20,$A43,'S4'!$E$6:$E$20,"Ambos")+SUMIFS('S5'!$I$6:$I$20,'S5'!$B$6:$B$20,$A43,'S5'!$E$6:$E$20,"Diego")+SUMIFS('S5'!$I$6:$I$20,'S5'!$B$6:$B$20,$A43,'S5'!$E$6:$E$20,"Ambos")+SUMIFS('S6'!$I$6:$I$17,'S6'!$B$6:$B$17,$A43,'S6'!$E$6:$E$17,"Diego")+SUMIFS('S6'!$I$6:$I$17,'S6'!$B$6:$B$17,$A43,'S6'!$E$6:$E$17,"Ambos")+SUMIFS('S7'!$I$6:$I$19,'S7'!$B$6:$B$19,$A43,'S7'!$E$6:$E$19,"Diego")+SUMIFS('S7'!$I$6:$I$19,'S7'!$B$6:$B$19,$A43,'S7'!$E$6:$E$19,"Ambos")+SUMIFS('S8'!$I$6:$I$23,'S8'!$B$6:$B$23,$A43,'S8'!$E$6:$E$23,"Diego")+SUMIFS('S8'!$I$6:$I$23,'S8'!$B$6:$B$23,$A43,'S8'!$E$6:$E$23,"Ambos")+SUMIFS('S9'!$I$6:$I$15,'S9'!$B$6:$B$15,$A43,'S9'!$E$6:$E$15,"Diego")+SUMIFS('S9'!$I$6:$I$15,'S9'!$B$6:$B$15,$A43,'S9'!$E$6:$E$15,"Ambos")+SUMIFS('S10'!$I$6:$I$13,'S10'!$B$6:$B$13,$A43,'S10'!$E$6:$E$13,"Diego")+SUMIFS('S10'!$I$6:$I$13,'S10'!$B$6:$B$13,$A43,'S10'!$E$6:$E$13,"Ambos")+SUMIFS('Holgura'!$I$6:$I$11,'Holgura'!$B$6:$B$11,$A43,'Holgura'!$E$6:$E$11,"Diego")+SUMIFS('Holgura'!$I$6:$I$11,'Holgura'!$B$6:$B$11,$A43,'Holgura'!$E$6:$E$11,"Ambos")+SUMIFS('Entrega'!$I$6:$I$9,'Entrega'!$B$6:$B$9,$A43,'Entrega'!$E$6:$E$9,"Diego")+SUMIFS('Entrega'!$I$6:$I$9,'Entrega'!$B$6:$B$9,$A43,'Entrega'!$E$6:$E$9,"Ambos")+SUMIFS('Defensa'!$I$6:$I$10,'Defensa'!$B$6:$B$10,$A43,'Defensa'!$E$6:$E$10,"Diego")+SUMIFS('Defensa'!$I$6:$I$10,'Defensa'!$B$6:$B$10,$A43,'Defensa'!$E$6:$E$10,"Ambos")</f>
+        <f>SUMIFS('S1'!$I$6:$I$32,'S1'!$B$6:$B$32,$A43,'S1'!$E$6:$E$32,"Diego")+SUMIFS('S1'!$I$6:$I$32,'S1'!$B$6:$B$32,$A43,'S1'!$E$6:$E$32,"Ambos")+SUMIFS('S2'!$I$6:$I$23,'S2'!$B$6:$B$23,$A43,'S2'!$E$6:$E$23,"Diego")+SUMIFS('S2'!$I$6:$I$23,'S2'!$B$6:$B$23,$A43,'S2'!$E$6:$E$23,"Ambos")+SUMIFS('S3'!$I$6:$I$24,'S3'!$B$6:$B$24,$A43,'S3'!$E$6:$E$24,"Diego")+SUMIFS('S3'!$I$6:$I$24,'S3'!$B$6:$B$24,$A43,'S3'!$E$6:$E$24,"Ambos")+SUMIFS('S4'!$I$6:$I$22,'S4'!$B$6:$B$22,$A43,'S4'!$E$6:$E$22,"Diego")+SUMIFS('S4'!$I$6:$I$22,'S4'!$B$6:$B$22,$A43,'S4'!$E$6:$E$22,"Ambos")+SUMIFS('S5'!$I$6:$I$20,'S5'!$B$6:$B$20,$A43,'S5'!$E$6:$E$20,"Diego")+SUMIFS('S5'!$I$6:$I$20,'S5'!$B$6:$B$20,$A43,'S5'!$E$6:$E$20,"Ambos")+SUMIFS('S6'!$I$6:$I$17,'S6'!$B$6:$B$17,$A43,'S6'!$E$6:$E$17,"Diego")+SUMIFS('S6'!$I$6:$I$17,'S6'!$B$6:$B$17,$A43,'S6'!$E$6:$E$17,"Ambos")+SUMIFS('S7'!$I$6:$I$19,'S7'!$B$6:$B$19,$A43,'S7'!$E$6:$E$19,"Diego")+SUMIFS('S7'!$I$6:$I$19,'S7'!$B$6:$B$19,$A43,'S7'!$E$6:$E$19,"Ambos")+SUMIFS('S8'!$I$6:$I$23,'S8'!$B$6:$B$23,$A43,'S8'!$E$6:$E$23,"Diego")+SUMIFS('S8'!$I$6:$I$23,'S8'!$B$6:$B$23,$A43,'S8'!$E$6:$E$23,"Ambos")+SUMIFS('S9'!$I$6:$I$15,'S9'!$B$6:$B$15,$A43,'S9'!$E$6:$E$15,"Diego")+SUMIFS('S9'!$I$6:$I$15,'S9'!$B$6:$B$15,$A43,'S9'!$E$6:$E$15,"Ambos")+SUMIFS('S10'!$I$6:$I$13,'S10'!$B$6:$B$13,$A43,'S10'!$E$6:$E$13,"Diego")+SUMIFS('S10'!$I$6:$I$13,'S10'!$B$6:$B$13,$A43,'S10'!$E$6:$E$13,"Ambos")+SUMIFS('Holgura'!$I$6:$I$11,'Holgura'!$B$6:$B$11,$A43,'Holgura'!$E$6:$E$11,"Diego")+SUMIFS('Holgura'!$I$6:$I$11,'Holgura'!$B$6:$B$11,$A43,'Holgura'!$E$6:$E$11,"Ambos")+SUMIFS('Entrega'!$I$6:$I$9,'Entrega'!$B$6:$B$9,$A43,'Entrega'!$E$6:$E$9,"Diego")+SUMIFS('Entrega'!$I$6:$I$9,'Entrega'!$B$6:$B$9,$A43,'Entrega'!$E$6:$E$9,"Ambos")+SUMIFS('Defensa'!$I$6:$I$10,'Defensa'!$B$6:$B$10,$A43,'Defensa'!$E$6:$E$10,"Diego")+SUMIFS('Defensa'!$I$6:$I$10,'Defensa'!$B$6:$B$10,$A43,'Defensa'!$E$6:$E$10,"Ambos")</f>
         <v/>
       </c>
       <c r="F43" s="21">
-        <f>COUNTIFS('S1'!$B$6:$B$32,$A43,'S1'!$E$6:$E$32,"Víctor")+COUNTIFS('S1'!$B$6:$B$32,$A43,'S1'!$E$6:$E$32,"Ambos")+COUNTIFS('S2'!$B$6:$B$23,$A43,'S2'!$E$6:$E$23,"Víctor")+COUNTIFS('S2'!$B$6:$B$23,$A43,'S2'!$E$6:$E$23,"Ambos")+COUNTIFS('S3'!$B$6:$B$19,$A43,'S3'!$E$6:$E$19,"Víctor")+COUNTIFS('S3'!$B$6:$B$19,$A43,'S3'!$E$6:$E$19,"Ambos")+COUNTIFS('S4'!$B$6:$B$20,$A43,'S4'!$E$6:$E$20,"Víctor")+COUNTIFS('S4'!$B$6:$B$20,$A43,'S4'!$E$6:$E$20,"Ambos")+COUNTIFS('S5'!$B$6:$B$20,$A43,'S5'!$E$6:$E$20,"Víctor")+COUNTIFS('S5'!$B$6:$B$20,$A43,'S5'!$E$6:$E$20,"Ambos")+COUNTIFS('S6'!$B$6:$B$17,$A43,'S6'!$E$6:$E$17,"Víctor")+COUNTIFS('S6'!$B$6:$B$17,$A43,'S6'!$E$6:$E$17,"Ambos")+COUNTIFS('S7'!$B$6:$B$19,$A43,'S7'!$E$6:$E$19,"Víctor")+COUNTIFS('S7'!$B$6:$B$19,$A43,'S7'!$E$6:$E$19,"Ambos")+COUNTIFS('S8'!$B$6:$B$23,$A43,'S8'!$E$6:$E$23,"Víctor")+COUNTIFS('S8'!$B$6:$B$23,$A43,'S8'!$E$6:$E$23,"Ambos")+COUNTIFS('S9'!$B$6:$B$15,$A43,'S9'!$E$6:$E$15,"Víctor")+COUNTIFS('S9'!$B$6:$B$15,$A43,'S9'!$E$6:$E$15,"Ambos")+COUNTIFS('S10'!$B$6:$B$13,$A43,'S10'!$E$6:$E$13,"Víctor")+COUNTIFS('S10'!$B$6:$B$13,$A43,'S10'!$E$6:$E$13,"Ambos")+COUNTIFS('Holgura'!$B$6:$B$11,$A43,'Holgura'!$E$6:$E$11,"Víctor")+COUNTIFS('Holgura'!$B$6:$B$11,$A43,'Holgura'!$E$6:$E$11,"Ambos")+COUNTIFS('Entrega'!$B$6:$B$9,$A43,'Entrega'!$E$6:$E$9,"Víctor")+COUNTIFS('Entrega'!$B$6:$B$9,$A43,'Entrega'!$E$6:$E$9,"Ambos")+COUNTIFS('Defensa'!$B$6:$B$10,$A43,'Defensa'!$E$6:$E$10,"Víctor")+COUNTIFS('Defensa'!$B$6:$B$10,$A43,'Defensa'!$E$6:$E$10,"Ambos")</f>
+        <f>COUNTIFS('S1'!$B$6:$B$32,$A43,'S1'!$E$6:$E$32,"Víctor")+COUNTIFS('S1'!$B$6:$B$32,$A43,'S1'!$E$6:$E$32,"Ambos")+COUNTIFS('S2'!$B$6:$B$23,$A43,'S2'!$E$6:$E$23,"Víctor")+COUNTIFS('S2'!$B$6:$B$23,$A43,'S2'!$E$6:$E$23,"Ambos")+COUNTIFS('S3'!$B$6:$B$24,$A43,'S3'!$E$6:$E$24,"Víctor")+COUNTIFS('S3'!$B$6:$B$24,$A43,'S3'!$E$6:$E$24,"Ambos")+COUNTIFS('S4'!$B$6:$B$22,$A43,'S4'!$E$6:$E$22,"Víctor")+COUNTIFS('S4'!$B$6:$B$22,$A43,'S4'!$E$6:$E$22,"Ambos")+COUNTIFS('S5'!$B$6:$B$20,$A43,'S5'!$E$6:$E$20,"Víctor")+COUNTIFS('S5'!$B$6:$B$20,$A43,'S5'!$E$6:$E$20,"Ambos")+COUNTIFS('S6'!$B$6:$B$17,$A43,'S6'!$E$6:$E$17,"Víctor")+COUNTIFS('S6'!$B$6:$B$17,$A43,'S6'!$E$6:$E$17,"Ambos")+COUNTIFS('S7'!$B$6:$B$19,$A43,'S7'!$E$6:$E$19,"Víctor")+COUNTIFS('S7'!$B$6:$B$19,$A43,'S7'!$E$6:$E$19,"Ambos")+COUNTIFS('S8'!$B$6:$B$23,$A43,'S8'!$E$6:$E$23,"Víctor")+COUNTIFS('S8'!$B$6:$B$23,$A43,'S8'!$E$6:$E$23,"Ambos")+COUNTIFS('S9'!$B$6:$B$15,$A43,'S9'!$E$6:$E$15,"Víctor")+COUNTIFS('S9'!$B$6:$B$15,$A43,'S9'!$E$6:$E$15,"Ambos")+COUNTIFS('S10'!$B$6:$B$13,$A43,'S10'!$E$6:$E$13,"Víctor")+COUNTIFS('S10'!$B$6:$B$13,$A43,'S10'!$E$6:$E$13,"Ambos")+COUNTIFS('Holgura'!$B$6:$B$11,$A43,'Holgura'!$E$6:$E$11,"Víctor")+COUNTIFS('Holgura'!$B$6:$B$11,$A43,'Holgura'!$E$6:$E$11,"Ambos")+COUNTIFS('Entrega'!$B$6:$B$9,$A43,'Entrega'!$E$6:$E$9,"Víctor")+COUNTIFS('Entrega'!$B$6:$B$9,$A43,'Entrega'!$E$6:$E$9,"Ambos")+COUNTIFS('Defensa'!$B$6:$B$10,$A43,'Defensa'!$E$6:$E$10,"Víctor")+COUNTIFS('Defensa'!$B$6:$B$10,$A43,'Defensa'!$E$6:$E$10,"Ambos")</f>
         <v/>
       </c>
       <c r="G43" s="21">
-        <f>COUNTIFS('S1'!$B$6:$B$32,$A43,'S1'!$E$6:$E$32,"Diego")+COUNTIFS('S1'!$B$6:$B$32,$A43,'S1'!$E$6:$E$32,"Ambos")+COUNTIFS('S2'!$B$6:$B$23,$A43,'S2'!$E$6:$E$23,"Diego")+COUNTIFS('S2'!$B$6:$B$23,$A43,'S2'!$E$6:$E$23,"Ambos")+COUNTIFS('S3'!$B$6:$B$19,$A43,'S3'!$E$6:$E$19,"Diego")+COUNTIFS('S3'!$B$6:$B$19,$A43,'S3'!$E$6:$E$19,"Ambos")+COUNTIFS('S4'!$B$6:$B$20,$A43,'S4'!$E$6:$E$20,"Diego")+COUNTIFS('S4'!$B$6:$B$20,$A43,'S4'!$E$6:$E$20,"Ambos")+COUNTIFS('S5'!$B$6:$B$20,$A43,'S5'!$E$6:$E$20,"Diego")+COUNTIFS('S5'!$B$6:$B$20,$A43,'S5'!$E$6:$E$20,"Ambos")+COUNTIFS('S6'!$B$6:$B$17,$A43,'S6'!$E$6:$E$17,"Diego")+COUNTIFS('S6'!$B$6:$B$17,$A43,'S6'!$E$6:$E$17,"Ambos")+COUNTIFS('S7'!$B$6:$B$19,$A43,'S7'!$E$6:$E$19,"Diego")+COUNTIFS('S7'!$B$6:$B$19,$A43,'S7'!$E$6:$E$19,"Ambos")+COUNTIFS('S8'!$B$6:$B$23,$A43,'S8'!$E$6:$E$23,"Diego")+COUNTIFS('S8'!$B$6:$B$23,$A43,'S8'!$E$6:$E$23,"Ambos")+COUNTIFS('S9'!$B$6:$B$15,$A43,'S9'!$E$6:$E$15,"Diego")+COUNTIFS('S9'!$B$6:$B$15,$A43,'S9'!$E$6:$E$15,"Ambos")+COUNTIFS('S10'!$B$6:$B$13,$A43,'S10'!$E$6:$E$13,"Diego")+COUNTIFS('S10'!$B$6:$B$13,$A43,'S10'!$E$6:$E$13,"Ambos")+COUNTIFS('Holgura'!$B$6:$B$11,$A43,'Holgura'!$E$6:$E$11,"Diego")+COUNTIFS('Holgura'!$B$6:$B$11,$A43,'Holgura'!$E$6:$E$11,"Ambos")+COUNTIFS('Entrega'!$B$6:$B$9,$A43,'Entrega'!$E$6:$E$9,"Diego")+COUNTIFS('Entrega'!$B$6:$B$9,$A43,'Entrega'!$E$6:$E$9,"Ambos")+COUNTIFS('Defensa'!$B$6:$B$10,$A43,'Defensa'!$E$6:$E$10,"Diego")+COUNTIFS('Defensa'!$B$6:$B$10,$A43,'Defensa'!$E$6:$E$10,"Ambos")</f>
+        <f>COUNTIFS('S1'!$B$6:$B$32,$A43,'S1'!$E$6:$E$32,"Diego")+COUNTIFS('S1'!$B$6:$B$32,$A43,'S1'!$E$6:$E$32,"Ambos")+COUNTIFS('S2'!$B$6:$B$23,$A43,'S2'!$E$6:$E$23,"Diego")+COUNTIFS('S2'!$B$6:$B$23,$A43,'S2'!$E$6:$E$23,"Ambos")+COUNTIFS('S3'!$B$6:$B$24,$A43,'S3'!$E$6:$E$24,"Diego")+COUNTIFS('S3'!$B$6:$B$24,$A43,'S3'!$E$6:$E$24,"Ambos")+COUNTIFS('S4'!$B$6:$B$22,$A43,'S4'!$E$6:$E$22,"Diego")+COUNTIFS('S4'!$B$6:$B$22,$A43,'S4'!$E$6:$E$22,"Ambos")+COUNTIFS('S5'!$B$6:$B$20,$A43,'S5'!$E$6:$E$20,"Diego")+COUNTIFS('S5'!$B$6:$B$20,$A43,'S5'!$E$6:$E$20,"Ambos")+COUNTIFS('S6'!$B$6:$B$17,$A43,'S6'!$E$6:$E$17,"Diego")+COUNTIFS('S6'!$B$6:$B$17,$A43,'S6'!$E$6:$E$17,"Ambos")+COUNTIFS('S7'!$B$6:$B$19,$A43,'S7'!$E$6:$E$19,"Diego")+COUNTIFS('S7'!$B$6:$B$19,$A43,'S7'!$E$6:$E$19,"Ambos")+COUNTIFS('S8'!$B$6:$B$23,$A43,'S8'!$E$6:$E$23,"Diego")+COUNTIFS('S8'!$B$6:$B$23,$A43,'S8'!$E$6:$E$23,"Ambos")+COUNTIFS('S9'!$B$6:$B$15,$A43,'S9'!$E$6:$E$15,"Diego")+COUNTIFS('S9'!$B$6:$B$15,$A43,'S9'!$E$6:$E$15,"Ambos")+COUNTIFS('S10'!$B$6:$B$13,$A43,'S10'!$E$6:$E$13,"Diego")+COUNTIFS('S10'!$B$6:$B$13,$A43,'S10'!$E$6:$E$13,"Ambos")+COUNTIFS('Holgura'!$B$6:$B$11,$A43,'Holgura'!$E$6:$E$11,"Diego")+COUNTIFS('Holgura'!$B$6:$B$11,$A43,'Holgura'!$E$6:$E$11,"Ambos")+COUNTIFS('Entrega'!$B$6:$B$9,$A43,'Entrega'!$E$6:$E$9,"Diego")+COUNTIFS('Entrega'!$B$6:$B$9,$A43,'Entrega'!$E$6:$E$9,"Ambos")+COUNTIFS('Defensa'!$B$6:$B$10,$A43,'Defensa'!$E$6:$E$10,"Diego")+COUNTIFS('Defensa'!$B$6:$B$10,$A43,'Defensa'!$E$6:$E$10,"Ambos")</f>
         <v/>
       </c>
     </row>
@@ -9811,19 +9832,19 @@
         <v/>
       </c>
       <c r="D44" s="21">
-        <f>SUMIFS('S1'!$I$6:$I$32,'S1'!$B$6:$B$32,$A44,'S1'!$E$6:$E$32,"Víctor")+SUMIFS('S1'!$I$6:$I$32,'S1'!$B$6:$B$32,$A44,'S1'!$E$6:$E$32,"Ambos")+SUMIFS('S2'!$I$6:$I$23,'S2'!$B$6:$B$23,$A44,'S2'!$E$6:$E$23,"Víctor")+SUMIFS('S2'!$I$6:$I$23,'S2'!$B$6:$B$23,$A44,'S2'!$E$6:$E$23,"Ambos")+SUMIFS('S3'!$I$6:$I$19,'S3'!$B$6:$B$19,$A44,'S3'!$E$6:$E$19,"Víctor")+SUMIFS('S3'!$I$6:$I$19,'S3'!$B$6:$B$19,$A44,'S3'!$E$6:$E$19,"Ambos")+SUMIFS('S4'!$I$6:$I$20,'S4'!$B$6:$B$20,$A44,'S4'!$E$6:$E$20,"Víctor")+SUMIFS('S4'!$I$6:$I$20,'S4'!$B$6:$B$20,$A44,'S4'!$E$6:$E$20,"Ambos")+SUMIFS('S5'!$I$6:$I$20,'S5'!$B$6:$B$20,$A44,'S5'!$E$6:$E$20,"Víctor")+SUMIFS('S5'!$I$6:$I$20,'S5'!$B$6:$B$20,$A44,'S5'!$E$6:$E$20,"Ambos")+SUMIFS('S6'!$I$6:$I$17,'S6'!$B$6:$B$17,$A44,'S6'!$E$6:$E$17,"Víctor")+SUMIFS('S6'!$I$6:$I$17,'S6'!$B$6:$B$17,$A44,'S6'!$E$6:$E$17,"Ambos")+SUMIFS('S7'!$I$6:$I$19,'S7'!$B$6:$B$19,$A44,'S7'!$E$6:$E$19,"Víctor")+SUMIFS('S7'!$I$6:$I$19,'S7'!$B$6:$B$19,$A44,'S7'!$E$6:$E$19,"Ambos")+SUMIFS('S8'!$I$6:$I$23,'S8'!$B$6:$B$23,$A44,'S8'!$E$6:$E$23,"Víctor")+SUMIFS('S8'!$I$6:$I$23,'S8'!$B$6:$B$23,$A44,'S8'!$E$6:$E$23,"Ambos")+SUMIFS('S9'!$I$6:$I$15,'S9'!$B$6:$B$15,$A44,'S9'!$E$6:$E$15,"Víctor")+SUMIFS('S9'!$I$6:$I$15,'S9'!$B$6:$B$15,$A44,'S9'!$E$6:$E$15,"Ambos")+SUMIFS('S10'!$I$6:$I$13,'S10'!$B$6:$B$13,$A44,'S10'!$E$6:$E$13,"Víctor")+SUMIFS('S10'!$I$6:$I$13,'S10'!$B$6:$B$13,$A44,'S10'!$E$6:$E$13,"Ambos")+SUMIFS('Holgura'!$I$6:$I$11,'Holgura'!$B$6:$B$11,$A44,'Holgura'!$E$6:$E$11,"Víctor")+SUMIFS('Holgura'!$I$6:$I$11,'Holgura'!$B$6:$B$11,$A44,'Holgura'!$E$6:$E$11,"Ambos")+SUMIFS('Entrega'!$I$6:$I$9,'Entrega'!$B$6:$B$9,$A44,'Entrega'!$E$6:$E$9,"Víctor")+SUMIFS('Entrega'!$I$6:$I$9,'Entrega'!$B$6:$B$9,$A44,'Entrega'!$E$6:$E$9,"Ambos")+SUMIFS('Defensa'!$I$6:$I$10,'Defensa'!$B$6:$B$10,$A44,'Defensa'!$E$6:$E$10,"Víctor")+SUMIFS('Defensa'!$I$6:$I$10,'Defensa'!$B$6:$B$10,$A44,'Defensa'!$E$6:$E$10,"Ambos")</f>
+        <f>SUMIFS('S1'!$I$6:$I$32,'S1'!$B$6:$B$32,$A44,'S1'!$E$6:$E$32,"Víctor")+SUMIFS('S1'!$I$6:$I$32,'S1'!$B$6:$B$32,$A44,'S1'!$E$6:$E$32,"Ambos")+SUMIFS('S2'!$I$6:$I$23,'S2'!$B$6:$B$23,$A44,'S2'!$E$6:$E$23,"Víctor")+SUMIFS('S2'!$I$6:$I$23,'S2'!$B$6:$B$23,$A44,'S2'!$E$6:$E$23,"Ambos")+SUMIFS('S3'!$I$6:$I$24,'S3'!$B$6:$B$24,$A44,'S3'!$E$6:$E$24,"Víctor")+SUMIFS('S3'!$I$6:$I$24,'S3'!$B$6:$B$24,$A44,'S3'!$E$6:$E$24,"Ambos")+SUMIFS('S4'!$I$6:$I$22,'S4'!$B$6:$B$22,$A44,'S4'!$E$6:$E$22,"Víctor")+SUMIFS('S4'!$I$6:$I$22,'S4'!$B$6:$B$22,$A44,'S4'!$E$6:$E$22,"Ambos")+SUMIFS('S5'!$I$6:$I$20,'S5'!$B$6:$B$20,$A44,'S5'!$E$6:$E$20,"Víctor")+SUMIFS('S5'!$I$6:$I$20,'S5'!$B$6:$B$20,$A44,'S5'!$E$6:$E$20,"Ambos")+SUMIFS('S6'!$I$6:$I$17,'S6'!$B$6:$B$17,$A44,'S6'!$E$6:$E$17,"Víctor")+SUMIFS('S6'!$I$6:$I$17,'S6'!$B$6:$B$17,$A44,'S6'!$E$6:$E$17,"Ambos")+SUMIFS('S7'!$I$6:$I$19,'S7'!$B$6:$B$19,$A44,'S7'!$E$6:$E$19,"Víctor")+SUMIFS('S7'!$I$6:$I$19,'S7'!$B$6:$B$19,$A44,'S7'!$E$6:$E$19,"Ambos")+SUMIFS('S8'!$I$6:$I$23,'S8'!$B$6:$B$23,$A44,'S8'!$E$6:$E$23,"Víctor")+SUMIFS('S8'!$I$6:$I$23,'S8'!$B$6:$B$23,$A44,'S8'!$E$6:$E$23,"Ambos")+SUMIFS('S9'!$I$6:$I$15,'S9'!$B$6:$B$15,$A44,'S9'!$E$6:$E$15,"Víctor")+SUMIFS('S9'!$I$6:$I$15,'S9'!$B$6:$B$15,$A44,'S9'!$E$6:$E$15,"Ambos")+SUMIFS('S10'!$I$6:$I$13,'S10'!$B$6:$B$13,$A44,'S10'!$E$6:$E$13,"Víctor")+SUMIFS('S10'!$I$6:$I$13,'S10'!$B$6:$B$13,$A44,'S10'!$E$6:$E$13,"Ambos")+SUMIFS('Holgura'!$I$6:$I$11,'Holgura'!$B$6:$B$11,$A44,'Holgura'!$E$6:$E$11,"Víctor")+SUMIFS('Holgura'!$I$6:$I$11,'Holgura'!$B$6:$B$11,$A44,'Holgura'!$E$6:$E$11,"Ambos")+SUMIFS('Entrega'!$I$6:$I$9,'Entrega'!$B$6:$B$9,$A44,'Entrega'!$E$6:$E$9,"Víctor")+SUMIFS('Entrega'!$I$6:$I$9,'Entrega'!$B$6:$B$9,$A44,'Entrega'!$E$6:$E$9,"Ambos")+SUMIFS('Defensa'!$I$6:$I$10,'Defensa'!$B$6:$B$10,$A44,'Defensa'!$E$6:$E$10,"Víctor")+SUMIFS('Defensa'!$I$6:$I$10,'Defensa'!$B$6:$B$10,$A44,'Defensa'!$E$6:$E$10,"Ambos")</f>
         <v/>
       </c>
       <c r="E44" s="21">
-        <f>SUMIFS('S1'!$I$6:$I$32,'S1'!$B$6:$B$32,$A44,'S1'!$E$6:$E$32,"Diego")+SUMIFS('S1'!$I$6:$I$32,'S1'!$B$6:$B$32,$A44,'S1'!$E$6:$E$32,"Ambos")+SUMIFS('S2'!$I$6:$I$23,'S2'!$B$6:$B$23,$A44,'S2'!$E$6:$E$23,"Diego")+SUMIFS('S2'!$I$6:$I$23,'S2'!$B$6:$B$23,$A44,'S2'!$E$6:$E$23,"Ambos")+SUMIFS('S3'!$I$6:$I$19,'S3'!$B$6:$B$19,$A44,'S3'!$E$6:$E$19,"Diego")+SUMIFS('S3'!$I$6:$I$19,'S3'!$B$6:$B$19,$A44,'S3'!$E$6:$E$19,"Ambos")+SUMIFS('S4'!$I$6:$I$20,'S4'!$B$6:$B$20,$A44,'S4'!$E$6:$E$20,"Diego")+SUMIFS('S4'!$I$6:$I$20,'S4'!$B$6:$B$20,$A44,'S4'!$E$6:$E$20,"Ambos")+SUMIFS('S5'!$I$6:$I$20,'S5'!$B$6:$B$20,$A44,'S5'!$E$6:$E$20,"Diego")+SUMIFS('S5'!$I$6:$I$20,'S5'!$B$6:$B$20,$A44,'S5'!$E$6:$E$20,"Ambos")+SUMIFS('S6'!$I$6:$I$17,'S6'!$B$6:$B$17,$A44,'S6'!$E$6:$E$17,"Diego")+SUMIFS('S6'!$I$6:$I$17,'S6'!$B$6:$B$17,$A44,'S6'!$E$6:$E$17,"Ambos")+SUMIFS('S7'!$I$6:$I$19,'S7'!$B$6:$B$19,$A44,'S7'!$E$6:$E$19,"Diego")+SUMIFS('S7'!$I$6:$I$19,'S7'!$B$6:$B$19,$A44,'S7'!$E$6:$E$19,"Ambos")+SUMIFS('S8'!$I$6:$I$23,'S8'!$B$6:$B$23,$A44,'S8'!$E$6:$E$23,"Diego")+SUMIFS('S8'!$I$6:$I$23,'S8'!$B$6:$B$23,$A44,'S8'!$E$6:$E$23,"Ambos")+SUMIFS('S9'!$I$6:$I$15,'S9'!$B$6:$B$15,$A44,'S9'!$E$6:$E$15,"Diego")+SUMIFS('S9'!$I$6:$I$15,'S9'!$B$6:$B$15,$A44,'S9'!$E$6:$E$15,"Ambos")+SUMIFS('S10'!$I$6:$I$13,'S10'!$B$6:$B$13,$A44,'S10'!$E$6:$E$13,"Diego")+SUMIFS('S10'!$I$6:$I$13,'S10'!$B$6:$B$13,$A44,'S10'!$E$6:$E$13,"Ambos")+SUMIFS('Holgura'!$I$6:$I$11,'Holgura'!$B$6:$B$11,$A44,'Holgura'!$E$6:$E$11,"Diego")+SUMIFS('Holgura'!$I$6:$I$11,'Holgura'!$B$6:$B$11,$A44,'Holgura'!$E$6:$E$11,"Ambos")+SUMIFS('Entrega'!$I$6:$I$9,'Entrega'!$B$6:$B$9,$A44,'Entrega'!$E$6:$E$9,"Diego")+SUMIFS('Entrega'!$I$6:$I$9,'Entrega'!$B$6:$B$9,$A44,'Entrega'!$E$6:$E$9,"Ambos")+SUMIFS('Defensa'!$I$6:$I$10,'Defensa'!$B$6:$B$10,$A44,'Defensa'!$E$6:$E$10,"Diego")+SUMIFS('Defensa'!$I$6:$I$10,'Defensa'!$B$6:$B$10,$A44,'Defensa'!$E$6:$E$10,"Ambos")</f>
+        <f>SUMIFS('S1'!$I$6:$I$32,'S1'!$B$6:$B$32,$A44,'S1'!$E$6:$E$32,"Diego")+SUMIFS('S1'!$I$6:$I$32,'S1'!$B$6:$B$32,$A44,'S1'!$E$6:$E$32,"Ambos")+SUMIFS('S2'!$I$6:$I$23,'S2'!$B$6:$B$23,$A44,'S2'!$E$6:$E$23,"Diego")+SUMIFS('S2'!$I$6:$I$23,'S2'!$B$6:$B$23,$A44,'S2'!$E$6:$E$23,"Ambos")+SUMIFS('S3'!$I$6:$I$24,'S3'!$B$6:$B$24,$A44,'S3'!$E$6:$E$24,"Diego")+SUMIFS('S3'!$I$6:$I$24,'S3'!$B$6:$B$24,$A44,'S3'!$E$6:$E$24,"Ambos")+SUMIFS('S4'!$I$6:$I$22,'S4'!$B$6:$B$22,$A44,'S4'!$E$6:$E$22,"Diego")+SUMIFS('S4'!$I$6:$I$22,'S4'!$B$6:$B$22,$A44,'S4'!$E$6:$E$22,"Ambos")+SUMIFS('S5'!$I$6:$I$20,'S5'!$B$6:$B$20,$A44,'S5'!$E$6:$E$20,"Diego")+SUMIFS('S5'!$I$6:$I$20,'S5'!$B$6:$B$20,$A44,'S5'!$E$6:$E$20,"Ambos")+SUMIFS('S6'!$I$6:$I$17,'S6'!$B$6:$B$17,$A44,'S6'!$E$6:$E$17,"Diego")+SUMIFS('S6'!$I$6:$I$17,'S6'!$B$6:$B$17,$A44,'S6'!$E$6:$E$17,"Ambos")+SUMIFS('S7'!$I$6:$I$19,'S7'!$B$6:$B$19,$A44,'S7'!$E$6:$E$19,"Diego")+SUMIFS('S7'!$I$6:$I$19,'S7'!$B$6:$B$19,$A44,'S7'!$E$6:$E$19,"Ambos")+SUMIFS('S8'!$I$6:$I$23,'S8'!$B$6:$B$23,$A44,'S8'!$E$6:$E$23,"Diego")+SUMIFS('S8'!$I$6:$I$23,'S8'!$B$6:$B$23,$A44,'S8'!$E$6:$E$23,"Ambos")+SUMIFS('S9'!$I$6:$I$15,'S9'!$B$6:$B$15,$A44,'S9'!$E$6:$E$15,"Diego")+SUMIFS('S9'!$I$6:$I$15,'S9'!$B$6:$B$15,$A44,'S9'!$E$6:$E$15,"Ambos")+SUMIFS('S10'!$I$6:$I$13,'S10'!$B$6:$B$13,$A44,'S10'!$E$6:$E$13,"Diego")+SUMIFS('S10'!$I$6:$I$13,'S10'!$B$6:$B$13,$A44,'S10'!$E$6:$E$13,"Ambos")+SUMIFS('Holgura'!$I$6:$I$11,'Holgura'!$B$6:$B$11,$A44,'Holgura'!$E$6:$E$11,"Diego")+SUMIFS('Holgura'!$I$6:$I$11,'Holgura'!$B$6:$B$11,$A44,'Holgura'!$E$6:$E$11,"Ambos")+SUMIFS('Entrega'!$I$6:$I$9,'Entrega'!$B$6:$B$9,$A44,'Entrega'!$E$6:$E$9,"Diego")+SUMIFS('Entrega'!$I$6:$I$9,'Entrega'!$B$6:$B$9,$A44,'Entrega'!$E$6:$E$9,"Ambos")+SUMIFS('Defensa'!$I$6:$I$10,'Defensa'!$B$6:$B$10,$A44,'Defensa'!$E$6:$E$10,"Diego")+SUMIFS('Defensa'!$I$6:$I$10,'Defensa'!$B$6:$B$10,$A44,'Defensa'!$E$6:$E$10,"Ambos")</f>
         <v/>
       </c>
       <c r="F44" s="21">
-        <f>COUNTIFS('S1'!$B$6:$B$32,$A44,'S1'!$E$6:$E$32,"Víctor")+COUNTIFS('S1'!$B$6:$B$32,$A44,'S1'!$E$6:$E$32,"Ambos")+COUNTIFS('S2'!$B$6:$B$23,$A44,'S2'!$E$6:$E$23,"Víctor")+COUNTIFS('S2'!$B$6:$B$23,$A44,'S2'!$E$6:$E$23,"Ambos")+COUNTIFS('S3'!$B$6:$B$19,$A44,'S3'!$E$6:$E$19,"Víctor")+COUNTIFS('S3'!$B$6:$B$19,$A44,'S3'!$E$6:$E$19,"Ambos")+COUNTIFS('S4'!$B$6:$B$20,$A44,'S4'!$E$6:$E$20,"Víctor")+COUNTIFS('S4'!$B$6:$B$20,$A44,'S4'!$E$6:$E$20,"Ambos")+COUNTIFS('S5'!$B$6:$B$20,$A44,'S5'!$E$6:$E$20,"Víctor")+COUNTIFS('S5'!$B$6:$B$20,$A44,'S5'!$E$6:$E$20,"Ambos")+COUNTIFS('S6'!$B$6:$B$17,$A44,'S6'!$E$6:$E$17,"Víctor")+COUNTIFS('S6'!$B$6:$B$17,$A44,'S6'!$E$6:$E$17,"Ambos")+COUNTIFS('S7'!$B$6:$B$19,$A44,'S7'!$E$6:$E$19,"Víctor")+COUNTIFS('S7'!$B$6:$B$19,$A44,'S7'!$E$6:$E$19,"Ambos")+COUNTIFS('S8'!$B$6:$B$23,$A44,'S8'!$E$6:$E$23,"Víctor")+COUNTIFS('S8'!$B$6:$B$23,$A44,'S8'!$E$6:$E$23,"Ambos")+COUNTIFS('S9'!$B$6:$B$15,$A44,'S9'!$E$6:$E$15,"Víctor")+COUNTIFS('S9'!$B$6:$B$15,$A44,'S9'!$E$6:$E$15,"Ambos")+COUNTIFS('S10'!$B$6:$B$13,$A44,'S10'!$E$6:$E$13,"Víctor")+COUNTIFS('S10'!$B$6:$B$13,$A44,'S10'!$E$6:$E$13,"Ambos")+COUNTIFS('Holgura'!$B$6:$B$11,$A44,'Holgura'!$E$6:$E$11,"Víctor")+COUNTIFS('Holgura'!$B$6:$B$11,$A44,'Holgura'!$E$6:$E$11,"Ambos")+COUNTIFS('Entrega'!$B$6:$B$9,$A44,'Entrega'!$E$6:$E$9,"Víctor")+COUNTIFS('Entrega'!$B$6:$B$9,$A44,'Entrega'!$E$6:$E$9,"Ambos")+COUNTIFS('Defensa'!$B$6:$B$10,$A44,'Defensa'!$E$6:$E$10,"Víctor")+COUNTIFS('Defensa'!$B$6:$B$10,$A44,'Defensa'!$E$6:$E$10,"Ambos")</f>
+        <f>COUNTIFS('S1'!$B$6:$B$32,$A44,'S1'!$E$6:$E$32,"Víctor")+COUNTIFS('S1'!$B$6:$B$32,$A44,'S1'!$E$6:$E$32,"Ambos")+COUNTIFS('S2'!$B$6:$B$23,$A44,'S2'!$E$6:$E$23,"Víctor")+COUNTIFS('S2'!$B$6:$B$23,$A44,'S2'!$E$6:$E$23,"Ambos")+COUNTIFS('S3'!$B$6:$B$24,$A44,'S3'!$E$6:$E$24,"Víctor")+COUNTIFS('S3'!$B$6:$B$24,$A44,'S3'!$E$6:$E$24,"Ambos")+COUNTIFS('S4'!$B$6:$B$22,$A44,'S4'!$E$6:$E$22,"Víctor")+COUNTIFS('S4'!$B$6:$B$22,$A44,'S4'!$E$6:$E$22,"Ambos")+COUNTIFS('S5'!$B$6:$B$20,$A44,'S5'!$E$6:$E$20,"Víctor")+COUNTIFS('S5'!$B$6:$B$20,$A44,'S5'!$E$6:$E$20,"Ambos")+COUNTIFS('S6'!$B$6:$B$17,$A44,'S6'!$E$6:$E$17,"Víctor")+COUNTIFS('S6'!$B$6:$B$17,$A44,'S6'!$E$6:$E$17,"Ambos")+COUNTIFS('S7'!$B$6:$B$19,$A44,'S7'!$E$6:$E$19,"Víctor")+COUNTIFS('S7'!$B$6:$B$19,$A44,'S7'!$E$6:$E$19,"Ambos")+COUNTIFS('S8'!$B$6:$B$23,$A44,'S8'!$E$6:$E$23,"Víctor")+COUNTIFS('S8'!$B$6:$B$23,$A44,'S8'!$E$6:$E$23,"Ambos")+COUNTIFS('S9'!$B$6:$B$15,$A44,'S9'!$E$6:$E$15,"Víctor")+COUNTIFS('S9'!$B$6:$B$15,$A44,'S9'!$E$6:$E$15,"Ambos")+COUNTIFS('S10'!$B$6:$B$13,$A44,'S10'!$E$6:$E$13,"Víctor")+COUNTIFS('S10'!$B$6:$B$13,$A44,'S10'!$E$6:$E$13,"Ambos")+COUNTIFS('Holgura'!$B$6:$B$11,$A44,'Holgura'!$E$6:$E$11,"Víctor")+COUNTIFS('Holgura'!$B$6:$B$11,$A44,'Holgura'!$E$6:$E$11,"Ambos")+COUNTIFS('Entrega'!$B$6:$B$9,$A44,'Entrega'!$E$6:$E$9,"Víctor")+COUNTIFS('Entrega'!$B$6:$B$9,$A44,'Entrega'!$E$6:$E$9,"Ambos")+COUNTIFS('Defensa'!$B$6:$B$10,$A44,'Defensa'!$E$6:$E$10,"Víctor")+COUNTIFS('Defensa'!$B$6:$B$10,$A44,'Defensa'!$E$6:$E$10,"Ambos")</f>
         <v/>
       </c>
       <c r="G44" s="21">
-        <f>COUNTIFS('S1'!$B$6:$B$32,$A44,'S1'!$E$6:$E$32,"Diego")+COUNTIFS('S1'!$B$6:$B$32,$A44,'S1'!$E$6:$E$32,"Ambos")+COUNTIFS('S2'!$B$6:$B$23,$A44,'S2'!$E$6:$E$23,"Diego")+COUNTIFS('S2'!$B$6:$B$23,$A44,'S2'!$E$6:$E$23,"Ambos")+COUNTIFS('S3'!$B$6:$B$19,$A44,'S3'!$E$6:$E$19,"Diego")+COUNTIFS('S3'!$B$6:$B$19,$A44,'S3'!$E$6:$E$19,"Ambos")+COUNTIFS('S4'!$B$6:$B$20,$A44,'S4'!$E$6:$E$20,"Diego")+COUNTIFS('S4'!$B$6:$B$20,$A44,'S4'!$E$6:$E$20,"Ambos")+COUNTIFS('S5'!$B$6:$B$20,$A44,'S5'!$E$6:$E$20,"Diego")+COUNTIFS('S5'!$B$6:$B$20,$A44,'S5'!$E$6:$E$20,"Ambos")+COUNTIFS('S6'!$B$6:$B$17,$A44,'S6'!$E$6:$E$17,"Diego")+COUNTIFS('S6'!$B$6:$B$17,$A44,'S6'!$E$6:$E$17,"Ambos")+COUNTIFS('S7'!$B$6:$B$19,$A44,'S7'!$E$6:$E$19,"Diego")+COUNTIFS('S7'!$B$6:$B$19,$A44,'S7'!$E$6:$E$19,"Ambos")+COUNTIFS('S8'!$B$6:$B$23,$A44,'S8'!$E$6:$E$23,"Diego")+COUNTIFS('S8'!$B$6:$B$23,$A44,'S8'!$E$6:$E$23,"Ambos")+COUNTIFS('S9'!$B$6:$B$15,$A44,'S9'!$E$6:$E$15,"Diego")+COUNTIFS('S9'!$B$6:$B$15,$A44,'S9'!$E$6:$E$15,"Ambos")+COUNTIFS('S10'!$B$6:$B$13,$A44,'S10'!$E$6:$E$13,"Diego")+COUNTIFS('S10'!$B$6:$B$13,$A44,'S10'!$E$6:$E$13,"Ambos")+COUNTIFS('Holgura'!$B$6:$B$11,$A44,'Holgura'!$E$6:$E$11,"Diego")+COUNTIFS('Holgura'!$B$6:$B$11,$A44,'Holgura'!$E$6:$E$11,"Ambos")+COUNTIFS('Entrega'!$B$6:$B$9,$A44,'Entrega'!$E$6:$E$9,"Diego")+COUNTIFS('Entrega'!$B$6:$B$9,$A44,'Entrega'!$E$6:$E$9,"Ambos")+COUNTIFS('Defensa'!$B$6:$B$10,$A44,'Defensa'!$E$6:$E$10,"Diego")+COUNTIFS('Defensa'!$B$6:$B$10,$A44,'Defensa'!$E$6:$E$10,"Ambos")</f>
+        <f>COUNTIFS('S1'!$B$6:$B$32,$A44,'S1'!$E$6:$E$32,"Diego")+COUNTIFS('S1'!$B$6:$B$32,$A44,'S1'!$E$6:$E$32,"Ambos")+COUNTIFS('S2'!$B$6:$B$23,$A44,'S2'!$E$6:$E$23,"Diego")+COUNTIFS('S2'!$B$6:$B$23,$A44,'S2'!$E$6:$E$23,"Ambos")+COUNTIFS('S3'!$B$6:$B$24,$A44,'S3'!$E$6:$E$24,"Diego")+COUNTIFS('S3'!$B$6:$B$24,$A44,'S3'!$E$6:$E$24,"Ambos")+COUNTIFS('S4'!$B$6:$B$22,$A44,'S4'!$E$6:$E$22,"Diego")+COUNTIFS('S4'!$B$6:$B$22,$A44,'S4'!$E$6:$E$22,"Ambos")+COUNTIFS('S5'!$B$6:$B$20,$A44,'S5'!$E$6:$E$20,"Diego")+COUNTIFS('S5'!$B$6:$B$20,$A44,'S5'!$E$6:$E$20,"Ambos")+COUNTIFS('S6'!$B$6:$B$17,$A44,'S6'!$E$6:$E$17,"Diego")+COUNTIFS('S6'!$B$6:$B$17,$A44,'S6'!$E$6:$E$17,"Ambos")+COUNTIFS('S7'!$B$6:$B$19,$A44,'S7'!$E$6:$E$19,"Diego")+COUNTIFS('S7'!$B$6:$B$19,$A44,'S7'!$E$6:$E$19,"Ambos")+COUNTIFS('S8'!$B$6:$B$23,$A44,'S8'!$E$6:$E$23,"Diego")+COUNTIFS('S8'!$B$6:$B$23,$A44,'S8'!$E$6:$E$23,"Ambos")+COUNTIFS('S9'!$B$6:$B$15,$A44,'S9'!$E$6:$E$15,"Diego")+COUNTIFS('S9'!$B$6:$B$15,$A44,'S9'!$E$6:$E$15,"Ambos")+COUNTIFS('S10'!$B$6:$B$13,$A44,'S10'!$E$6:$E$13,"Diego")+COUNTIFS('S10'!$B$6:$B$13,$A44,'S10'!$E$6:$E$13,"Ambos")+COUNTIFS('Holgura'!$B$6:$B$11,$A44,'Holgura'!$E$6:$E$11,"Diego")+COUNTIFS('Holgura'!$B$6:$B$11,$A44,'Holgura'!$E$6:$E$11,"Ambos")+COUNTIFS('Entrega'!$B$6:$B$9,$A44,'Entrega'!$E$6:$E$9,"Diego")+COUNTIFS('Entrega'!$B$6:$B$9,$A44,'Entrega'!$E$6:$E$9,"Ambos")+COUNTIFS('Defensa'!$B$6:$B$10,$A44,'Defensa'!$E$6:$E$10,"Diego")+COUNTIFS('Defensa'!$B$6:$B$10,$A44,'Defensa'!$E$6:$E$10,"Ambos")</f>
         <v/>
       </c>
     </row>
@@ -9840,19 +9861,19 @@
         <v/>
       </c>
       <c r="D45" s="21">
-        <f>SUMIFS('S1'!$I$6:$I$32,'S1'!$B$6:$B$32,$A45,'S1'!$E$6:$E$32,"Víctor")+SUMIFS('S1'!$I$6:$I$32,'S1'!$B$6:$B$32,$A45,'S1'!$E$6:$E$32,"Ambos")+SUMIFS('S2'!$I$6:$I$23,'S2'!$B$6:$B$23,$A45,'S2'!$E$6:$E$23,"Víctor")+SUMIFS('S2'!$I$6:$I$23,'S2'!$B$6:$B$23,$A45,'S2'!$E$6:$E$23,"Ambos")+SUMIFS('S3'!$I$6:$I$19,'S3'!$B$6:$B$19,$A45,'S3'!$E$6:$E$19,"Víctor")+SUMIFS('S3'!$I$6:$I$19,'S3'!$B$6:$B$19,$A45,'S3'!$E$6:$E$19,"Ambos")+SUMIFS('S4'!$I$6:$I$20,'S4'!$B$6:$B$20,$A45,'S4'!$E$6:$E$20,"Víctor")+SUMIFS('S4'!$I$6:$I$20,'S4'!$B$6:$B$20,$A45,'S4'!$E$6:$E$20,"Ambos")+SUMIFS('S5'!$I$6:$I$20,'S5'!$B$6:$B$20,$A45,'S5'!$E$6:$E$20,"Víctor")+SUMIFS('S5'!$I$6:$I$20,'S5'!$B$6:$B$20,$A45,'S5'!$E$6:$E$20,"Ambos")+SUMIFS('S6'!$I$6:$I$17,'S6'!$B$6:$B$17,$A45,'S6'!$E$6:$E$17,"Víctor")+SUMIFS('S6'!$I$6:$I$17,'S6'!$B$6:$B$17,$A45,'S6'!$E$6:$E$17,"Ambos")+SUMIFS('S7'!$I$6:$I$19,'S7'!$B$6:$B$19,$A45,'S7'!$E$6:$E$19,"Víctor")+SUMIFS('S7'!$I$6:$I$19,'S7'!$B$6:$B$19,$A45,'S7'!$E$6:$E$19,"Ambos")+SUMIFS('S8'!$I$6:$I$23,'S8'!$B$6:$B$23,$A45,'S8'!$E$6:$E$23,"Víctor")+SUMIFS('S8'!$I$6:$I$23,'S8'!$B$6:$B$23,$A45,'S8'!$E$6:$E$23,"Ambos")+SUMIFS('S9'!$I$6:$I$15,'S9'!$B$6:$B$15,$A45,'S9'!$E$6:$E$15,"Víctor")+SUMIFS('S9'!$I$6:$I$15,'S9'!$B$6:$B$15,$A45,'S9'!$E$6:$E$15,"Ambos")+SUMIFS('S10'!$I$6:$I$13,'S10'!$B$6:$B$13,$A45,'S10'!$E$6:$E$13,"Víctor")+SUMIFS('S10'!$I$6:$I$13,'S10'!$B$6:$B$13,$A45,'S10'!$E$6:$E$13,"Ambos")+SUMIFS('Holgura'!$I$6:$I$11,'Holgura'!$B$6:$B$11,$A45,'Holgura'!$E$6:$E$11,"Víctor")+SUMIFS('Holgura'!$I$6:$I$11,'Holgura'!$B$6:$B$11,$A45,'Holgura'!$E$6:$E$11,"Ambos")+SUMIFS('Entrega'!$I$6:$I$9,'Entrega'!$B$6:$B$9,$A45,'Entrega'!$E$6:$E$9,"Víctor")+SUMIFS('Entrega'!$I$6:$I$9,'Entrega'!$B$6:$B$9,$A45,'Entrega'!$E$6:$E$9,"Ambos")+SUMIFS('Defensa'!$I$6:$I$10,'Defensa'!$B$6:$B$10,$A45,'Defensa'!$E$6:$E$10,"Víctor")+SUMIFS('Defensa'!$I$6:$I$10,'Defensa'!$B$6:$B$10,$A45,'Defensa'!$E$6:$E$10,"Ambos")</f>
+        <f>SUMIFS('S1'!$I$6:$I$32,'S1'!$B$6:$B$32,$A45,'S1'!$E$6:$E$32,"Víctor")+SUMIFS('S1'!$I$6:$I$32,'S1'!$B$6:$B$32,$A45,'S1'!$E$6:$E$32,"Ambos")+SUMIFS('S2'!$I$6:$I$23,'S2'!$B$6:$B$23,$A45,'S2'!$E$6:$E$23,"Víctor")+SUMIFS('S2'!$I$6:$I$23,'S2'!$B$6:$B$23,$A45,'S2'!$E$6:$E$23,"Ambos")+SUMIFS('S3'!$I$6:$I$24,'S3'!$B$6:$B$24,$A45,'S3'!$E$6:$E$24,"Víctor")+SUMIFS('S3'!$I$6:$I$24,'S3'!$B$6:$B$24,$A45,'S3'!$E$6:$E$24,"Ambos")+SUMIFS('S4'!$I$6:$I$22,'S4'!$B$6:$B$22,$A45,'S4'!$E$6:$E$22,"Víctor")+SUMIFS('S4'!$I$6:$I$22,'S4'!$B$6:$B$22,$A45,'S4'!$E$6:$E$22,"Ambos")+SUMIFS('S5'!$I$6:$I$20,'S5'!$B$6:$B$20,$A45,'S5'!$E$6:$E$20,"Víctor")+SUMIFS('S5'!$I$6:$I$20,'S5'!$B$6:$B$20,$A45,'S5'!$E$6:$E$20,"Ambos")+SUMIFS('S6'!$I$6:$I$17,'S6'!$B$6:$B$17,$A45,'S6'!$E$6:$E$17,"Víctor")+SUMIFS('S6'!$I$6:$I$17,'S6'!$B$6:$B$17,$A45,'S6'!$E$6:$E$17,"Ambos")+SUMIFS('S7'!$I$6:$I$19,'S7'!$B$6:$B$19,$A45,'S7'!$E$6:$E$19,"Víctor")+SUMIFS('S7'!$I$6:$I$19,'S7'!$B$6:$B$19,$A45,'S7'!$E$6:$E$19,"Ambos")+SUMIFS('S8'!$I$6:$I$23,'S8'!$B$6:$B$23,$A45,'S8'!$E$6:$E$23,"Víctor")+SUMIFS('S8'!$I$6:$I$23,'S8'!$B$6:$B$23,$A45,'S8'!$E$6:$E$23,"Ambos")+SUMIFS('S9'!$I$6:$I$15,'S9'!$B$6:$B$15,$A45,'S9'!$E$6:$E$15,"Víctor")+SUMIFS('S9'!$I$6:$I$15,'S9'!$B$6:$B$15,$A45,'S9'!$E$6:$E$15,"Ambos")+SUMIFS('S10'!$I$6:$I$13,'S10'!$B$6:$B$13,$A45,'S10'!$E$6:$E$13,"Víctor")+SUMIFS('S10'!$I$6:$I$13,'S10'!$B$6:$B$13,$A45,'S10'!$E$6:$E$13,"Ambos")+SUMIFS('Holgura'!$I$6:$I$11,'Holgura'!$B$6:$B$11,$A45,'Holgura'!$E$6:$E$11,"Víctor")+SUMIFS('Holgura'!$I$6:$I$11,'Holgura'!$B$6:$B$11,$A45,'Holgura'!$E$6:$E$11,"Ambos")+SUMIFS('Entrega'!$I$6:$I$9,'Entrega'!$B$6:$B$9,$A45,'Entrega'!$E$6:$E$9,"Víctor")+SUMIFS('Entrega'!$I$6:$I$9,'Entrega'!$B$6:$B$9,$A45,'Entrega'!$E$6:$E$9,"Ambos")+SUMIFS('Defensa'!$I$6:$I$10,'Defensa'!$B$6:$B$10,$A45,'Defensa'!$E$6:$E$10,"Víctor")+SUMIFS('Defensa'!$I$6:$I$10,'Defensa'!$B$6:$B$10,$A45,'Defensa'!$E$6:$E$10,"Ambos")</f>
         <v/>
       </c>
       <c r="E45" s="21">
-        <f>SUMIFS('S1'!$I$6:$I$32,'S1'!$B$6:$B$32,$A45,'S1'!$E$6:$E$32,"Diego")+SUMIFS('S1'!$I$6:$I$32,'S1'!$B$6:$B$32,$A45,'S1'!$E$6:$E$32,"Ambos")+SUMIFS('S2'!$I$6:$I$23,'S2'!$B$6:$B$23,$A45,'S2'!$E$6:$E$23,"Diego")+SUMIFS('S2'!$I$6:$I$23,'S2'!$B$6:$B$23,$A45,'S2'!$E$6:$E$23,"Ambos")+SUMIFS('S3'!$I$6:$I$19,'S3'!$B$6:$B$19,$A45,'S3'!$E$6:$E$19,"Diego")+SUMIFS('S3'!$I$6:$I$19,'S3'!$B$6:$B$19,$A45,'S3'!$E$6:$E$19,"Ambos")+SUMIFS('S4'!$I$6:$I$20,'S4'!$B$6:$B$20,$A45,'S4'!$E$6:$E$20,"Diego")+SUMIFS('S4'!$I$6:$I$20,'S4'!$B$6:$B$20,$A45,'S4'!$E$6:$E$20,"Ambos")+SUMIFS('S5'!$I$6:$I$20,'S5'!$B$6:$B$20,$A45,'S5'!$E$6:$E$20,"Diego")+SUMIFS('S5'!$I$6:$I$20,'S5'!$B$6:$B$20,$A45,'S5'!$E$6:$E$20,"Ambos")+SUMIFS('S6'!$I$6:$I$17,'S6'!$B$6:$B$17,$A45,'S6'!$E$6:$E$17,"Diego")+SUMIFS('S6'!$I$6:$I$17,'S6'!$B$6:$B$17,$A45,'S6'!$E$6:$E$17,"Ambos")+SUMIFS('S7'!$I$6:$I$19,'S7'!$B$6:$B$19,$A45,'S7'!$E$6:$E$19,"Diego")+SUMIFS('S7'!$I$6:$I$19,'S7'!$B$6:$B$19,$A45,'S7'!$E$6:$E$19,"Ambos")+SUMIFS('S8'!$I$6:$I$23,'S8'!$B$6:$B$23,$A45,'S8'!$E$6:$E$23,"Diego")+SUMIFS('S8'!$I$6:$I$23,'S8'!$B$6:$B$23,$A45,'S8'!$E$6:$E$23,"Ambos")+SUMIFS('S9'!$I$6:$I$15,'S9'!$B$6:$B$15,$A45,'S9'!$E$6:$E$15,"Diego")+SUMIFS('S9'!$I$6:$I$15,'S9'!$B$6:$B$15,$A45,'S9'!$E$6:$E$15,"Ambos")+SUMIFS('S10'!$I$6:$I$13,'S10'!$B$6:$B$13,$A45,'S10'!$E$6:$E$13,"Diego")+SUMIFS('S10'!$I$6:$I$13,'S10'!$B$6:$B$13,$A45,'S10'!$E$6:$E$13,"Ambos")+SUMIFS('Holgura'!$I$6:$I$11,'Holgura'!$B$6:$B$11,$A45,'Holgura'!$E$6:$E$11,"Diego")+SUMIFS('Holgura'!$I$6:$I$11,'Holgura'!$B$6:$B$11,$A45,'Holgura'!$E$6:$E$11,"Ambos")+SUMIFS('Entrega'!$I$6:$I$9,'Entrega'!$B$6:$B$9,$A45,'Entrega'!$E$6:$E$9,"Diego")+SUMIFS('Entrega'!$I$6:$I$9,'Entrega'!$B$6:$B$9,$A45,'Entrega'!$E$6:$E$9,"Ambos")+SUMIFS('Defensa'!$I$6:$I$10,'Defensa'!$B$6:$B$10,$A45,'Defensa'!$E$6:$E$10,"Diego")+SUMIFS('Defensa'!$I$6:$I$10,'Defensa'!$B$6:$B$10,$A45,'Defensa'!$E$6:$E$10,"Ambos")</f>
+        <f>SUMIFS('S1'!$I$6:$I$32,'S1'!$B$6:$B$32,$A45,'S1'!$E$6:$E$32,"Diego")+SUMIFS('S1'!$I$6:$I$32,'S1'!$B$6:$B$32,$A45,'S1'!$E$6:$E$32,"Ambos")+SUMIFS('S2'!$I$6:$I$23,'S2'!$B$6:$B$23,$A45,'S2'!$E$6:$E$23,"Diego")+SUMIFS('S2'!$I$6:$I$23,'S2'!$B$6:$B$23,$A45,'S2'!$E$6:$E$23,"Ambos")+SUMIFS('S3'!$I$6:$I$24,'S3'!$B$6:$B$24,$A45,'S3'!$E$6:$E$24,"Diego")+SUMIFS('S3'!$I$6:$I$24,'S3'!$B$6:$B$24,$A45,'S3'!$E$6:$E$24,"Ambos")+SUMIFS('S4'!$I$6:$I$22,'S4'!$B$6:$B$22,$A45,'S4'!$E$6:$E$22,"Diego")+SUMIFS('S4'!$I$6:$I$22,'S4'!$B$6:$B$22,$A45,'S4'!$E$6:$E$22,"Ambos")+SUMIFS('S5'!$I$6:$I$20,'S5'!$B$6:$B$20,$A45,'S5'!$E$6:$E$20,"Diego")+SUMIFS('S5'!$I$6:$I$20,'S5'!$B$6:$B$20,$A45,'S5'!$E$6:$E$20,"Ambos")+SUMIFS('S6'!$I$6:$I$17,'S6'!$B$6:$B$17,$A45,'S6'!$E$6:$E$17,"Diego")+SUMIFS('S6'!$I$6:$I$17,'S6'!$B$6:$B$17,$A45,'S6'!$E$6:$E$17,"Ambos")+SUMIFS('S7'!$I$6:$I$19,'S7'!$B$6:$B$19,$A45,'S7'!$E$6:$E$19,"Diego")+SUMIFS('S7'!$I$6:$I$19,'S7'!$B$6:$B$19,$A45,'S7'!$E$6:$E$19,"Ambos")+SUMIFS('S8'!$I$6:$I$23,'S8'!$B$6:$B$23,$A45,'S8'!$E$6:$E$23,"Diego")+SUMIFS('S8'!$I$6:$I$23,'S8'!$B$6:$B$23,$A45,'S8'!$E$6:$E$23,"Ambos")+SUMIFS('S9'!$I$6:$I$15,'S9'!$B$6:$B$15,$A45,'S9'!$E$6:$E$15,"Diego")+SUMIFS('S9'!$I$6:$I$15,'S9'!$B$6:$B$15,$A45,'S9'!$E$6:$E$15,"Ambos")+SUMIFS('S10'!$I$6:$I$13,'S10'!$B$6:$B$13,$A45,'S10'!$E$6:$E$13,"Diego")+SUMIFS('S10'!$I$6:$I$13,'S10'!$B$6:$B$13,$A45,'S10'!$E$6:$E$13,"Ambos")+SUMIFS('Holgura'!$I$6:$I$11,'Holgura'!$B$6:$B$11,$A45,'Holgura'!$E$6:$E$11,"Diego")+SUMIFS('Holgura'!$I$6:$I$11,'Holgura'!$B$6:$B$11,$A45,'Holgura'!$E$6:$E$11,"Ambos")+SUMIFS('Entrega'!$I$6:$I$9,'Entrega'!$B$6:$B$9,$A45,'Entrega'!$E$6:$E$9,"Diego")+SUMIFS('Entrega'!$I$6:$I$9,'Entrega'!$B$6:$B$9,$A45,'Entrega'!$E$6:$E$9,"Ambos")+SUMIFS('Defensa'!$I$6:$I$10,'Defensa'!$B$6:$B$10,$A45,'Defensa'!$E$6:$E$10,"Diego")+SUMIFS('Defensa'!$I$6:$I$10,'Defensa'!$B$6:$B$10,$A45,'Defensa'!$E$6:$E$10,"Ambos")</f>
         <v/>
       </c>
       <c r="F45" s="21">
-        <f>COUNTIFS('S1'!$B$6:$B$32,$A45,'S1'!$E$6:$E$32,"Víctor")+COUNTIFS('S1'!$B$6:$B$32,$A45,'S1'!$E$6:$E$32,"Ambos")+COUNTIFS('S2'!$B$6:$B$23,$A45,'S2'!$E$6:$E$23,"Víctor")+COUNTIFS('S2'!$B$6:$B$23,$A45,'S2'!$E$6:$E$23,"Ambos")+COUNTIFS('S3'!$B$6:$B$19,$A45,'S3'!$E$6:$E$19,"Víctor")+COUNTIFS('S3'!$B$6:$B$19,$A45,'S3'!$E$6:$E$19,"Ambos")+COUNTIFS('S4'!$B$6:$B$20,$A45,'S4'!$E$6:$E$20,"Víctor")+COUNTIFS('S4'!$B$6:$B$20,$A45,'S4'!$E$6:$E$20,"Ambos")+COUNTIFS('S5'!$B$6:$B$20,$A45,'S5'!$E$6:$E$20,"Víctor")+COUNTIFS('S5'!$B$6:$B$20,$A45,'S5'!$E$6:$E$20,"Ambos")+COUNTIFS('S6'!$B$6:$B$17,$A45,'S6'!$E$6:$E$17,"Víctor")+COUNTIFS('S6'!$B$6:$B$17,$A45,'S6'!$E$6:$E$17,"Ambos")+COUNTIFS('S7'!$B$6:$B$19,$A45,'S7'!$E$6:$E$19,"Víctor")+COUNTIFS('S7'!$B$6:$B$19,$A45,'S7'!$E$6:$E$19,"Ambos")+COUNTIFS('S8'!$B$6:$B$23,$A45,'S8'!$E$6:$E$23,"Víctor")+COUNTIFS('S8'!$B$6:$B$23,$A45,'S8'!$E$6:$E$23,"Ambos")+COUNTIFS('S9'!$B$6:$B$15,$A45,'S9'!$E$6:$E$15,"Víctor")+COUNTIFS('S9'!$B$6:$B$15,$A45,'S9'!$E$6:$E$15,"Ambos")+COUNTIFS('S10'!$B$6:$B$13,$A45,'S10'!$E$6:$E$13,"Víctor")+COUNTIFS('S10'!$B$6:$B$13,$A45,'S10'!$E$6:$E$13,"Ambos")+COUNTIFS('Holgura'!$B$6:$B$11,$A45,'Holgura'!$E$6:$E$11,"Víctor")+COUNTIFS('Holgura'!$B$6:$B$11,$A45,'Holgura'!$E$6:$E$11,"Ambos")+COUNTIFS('Entrega'!$B$6:$B$9,$A45,'Entrega'!$E$6:$E$9,"Víctor")+COUNTIFS('Entrega'!$B$6:$B$9,$A45,'Entrega'!$E$6:$E$9,"Ambos")+COUNTIFS('Defensa'!$B$6:$B$10,$A45,'Defensa'!$E$6:$E$10,"Víctor")+COUNTIFS('Defensa'!$B$6:$B$10,$A45,'Defensa'!$E$6:$E$10,"Ambos")</f>
+        <f>COUNTIFS('S1'!$B$6:$B$32,$A45,'S1'!$E$6:$E$32,"Víctor")+COUNTIFS('S1'!$B$6:$B$32,$A45,'S1'!$E$6:$E$32,"Ambos")+COUNTIFS('S2'!$B$6:$B$23,$A45,'S2'!$E$6:$E$23,"Víctor")+COUNTIFS('S2'!$B$6:$B$23,$A45,'S2'!$E$6:$E$23,"Ambos")+COUNTIFS('S3'!$B$6:$B$24,$A45,'S3'!$E$6:$E$24,"Víctor")+COUNTIFS('S3'!$B$6:$B$24,$A45,'S3'!$E$6:$E$24,"Ambos")+COUNTIFS('S4'!$B$6:$B$22,$A45,'S4'!$E$6:$E$22,"Víctor")+COUNTIFS('S4'!$B$6:$B$22,$A45,'S4'!$E$6:$E$22,"Ambos")+COUNTIFS('S5'!$B$6:$B$20,$A45,'S5'!$E$6:$E$20,"Víctor")+COUNTIFS('S5'!$B$6:$B$20,$A45,'S5'!$E$6:$E$20,"Ambos")+COUNTIFS('S6'!$B$6:$B$17,$A45,'S6'!$E$6:$E$17,"Víctor")+COUNTIFS('S6'!$B$6:$B$17,$A45,'S6'!$E$6:$E$17,"Ambos")+COUNTIFS('S7'!$B$6:$B$19,$A45,'S7'!$E$6:$E$19,"Víctor")+COUNTIFS('S7'!$B$6:$B$19,$A45,'S7'!$E$6:$E$19,"Ambos")+COUNTIFS('S8'!$B$6:$B$23,$A45,'S8'!$E$6:$E$23,"Víctor")+COUNTIFS('S8'!$B$6:$B$23,$A45,'S8'!$E$6:$E$23,"Ambos")+COUNTIFS('S9'!$B$6:$B$15,$A45,'S9'!$E$6:$E$15,"Víctor")+COUNTIFS('S9'!$B$6:$B$15,$A45,'S9'!$E$6:$E$15,"Ambos")+COUNTIFS('S10'!$B$6:$B$13,$A45,'S10'!$E$6:$E$13,"Víctor")+COUNTIFS('S10'!$B$6:$B$13,$A45,'S10'!$E$6:$E$13,"Ambos")+COUNTIFS('Holgura'!$B$6:$B$11,$A45,'Holgura'!$E$6:$E$11,"Víctor")+COUNTIFS('Holgura'!$B$6:$B$11,$A45,'Holgura'!$E$6:$E$11,"Ambos")+COUNTIFS('Entrega'!$B$6:$B$9,$A45,'Entrega'!$E$6:$E$9,"Víctor")+COUNTIFS('Entrega'!$B$6:$B$9,$A45,'Entrega'!$E$6:$E$9,"Ambos")+COUNTIFS('Defensa'!$B$6:$B$10,$A45,'Defensa'!$E$6:$E$10,"Víctor")+COUNTIFS('Defensa'!$B$6:$B$10,$A45,'Defensa'!$E$6:$E$10,"Ambos")</f>
         <v/>
       </c>
       <c r="G45" s="21">
-        <f>COUNTIFS('S1'!$B$6:$B$32,$A45,'S1'!$E$6:$E$32,"Diego")+COUNTIFS('S1'!$B$6:$B$32,$A45,'S1'!$E$6:$E$32,"Ambos")+COUNTIFS('S2'!$B$6:$B$23,$A45,'S2'!$E$6:$E$23,"Diego")+COUNTIFS('S2'!$B$6:$B$23,$A45,'S2'!$E$6:$E$23,"Ambos")+COUNTIFS('S3'!$B$6:$B$19,$A45,'S3'!$E$6:$E$19,"Diego")+COUNTIFS('S3'!$B$6:$B$19,$A45,'S3'!$E$6:$E$19,"Ambos")+COUNTIFS('S4'!$B$6:$B$20,$A45,'S4'!$E$6:$E$20,"Diego")+COUNTIFS('S4'!$B$6:$B$20,$A45,'S4'!$E$6:$E$20,"Ambos")+COUNTIFS('S5'!$B$6:$B$20,$A45,'S5'!$E$6:$E$20,"Diego")+COUNTIFS('S5'!$B$6:$B$20,$A45,'S5'!$E$6:$E$20,"Ambos")+COUNTIFS('S6'!$B$6:$B$17,$A45,'S6'!$E$6:$E$17,"Diego")+COUNTIFS('S6'!$B$6:$B$17,$A45,'S6'!$E$6:$E$17,"Ambos")+COUNTIFS('S7'!$B$6:$B$19,$A45,'S7'!$E$6:$E$19,"Diego")+COUNTIFS('S7'!$B$6:$B$19,$A45,'S7'!$E$6:$E$19,"Ambos")+COUNTIFS('S8'!$B$6:$B$23,$A45,'S8'!$E$6:$E$23,"Diego")+COUNTIFS('S8'!$B$6:$B$23,$A45,'S8'!$E$6:$E$23,"Ambos")+COUNTIFS('S9'!$B$6:$B$15,$A45,'S9'!$E$6:$E$15,"Diego")+COUNTIFS('S9'!$B$6:$B$15,$A45,'S9'!$E$6:$E$15,"Ambos")+COUNTIFS('S10'!$B$6:$B$13,$A45,'S10'!$E$6:$E$13,"Diego")+COUNTIFS('S10'!$B$6:$B$13,$A45,'S10'!$E$6:$E$13,"Ambos")+COUNTIFS('Holgura'!$B$6:$B$11,$A45,'Holgura'!$E$6:$E$11,"Diego")+COUNTIFS('Holgura'!$B$6:$B$11,$A45,'Holgura'!$E$6:$E$11,"Ambos")+COUNTIFS('Entrega'!$B$6:$B$9,$A45,'Entrega'!$E$6:$E$9,"Diego")+COUNTIFS('Entrega'!$B$6:$B$9,$A45,'Entrega'!$E$6:$E$9,"Ambos")+COUNTIFS('Defensa'!$B$6:$B$10,$A45,'Defensa'!$E$6:$E$10,"Diego")+COUNTIFS('Defensa'!$B$6:$B$10,$A45,'Defensa'!$E$6:$E$10,"Ambos")</f>
+        <f>COUNTIFS('S1'!$B$6:$B$32,$A45,'S1'!$E$6:$E$32,"Diego")+COUNTIFS('S1'!$B$6:$B$32,$A45,'S1'!$E$6:$E$32,"Ambos")+COUNTIFS('S2'!$B$6:$B$23,$A45,'S2'!$E$6:$E$23,"Diego")+COUNTIFS('S2'!$B$6:$B$23,$A45,'S2'!$E$6:$E$23,"Ambos")+COUNTIFS('S3'!$B$6:$B$24,$A45,'S3'!$E$6:$E$24,"Diego")+COUNTIFS('S3'!$B$6:$B$24,$A45,'S3'!$E$6:$E$24,"Ambos")+COUNTIFS('S4'!$B$6:$B$22,$A45,'S4'!$E$6:$E$22,"Diego")+COUNTIFS('S4'!$B$6:$B$22,$A45,'S4'!$E$6:$E$22,"Ambos")+COUNTIFS('S5'!$B$6:$B$20,$A45,'S5'!$E$6:$E$20,"Diego")+COUNTIFS('S5'!$B$6:$B$20,$A45,'S5'!$E$6:$E$20,"Ambos")+COUNTIFS('S6'!$B$6:$B$17,$A45,'S6'!$E$6:$E$17,"Diego")+COUNTIFS('S6'!$B$6:$B$17,$A45,'S6'!$E$6:$E$17,"Ambos")+COUNTIFS('S7'!$B$6:$B$19,$A45,'S7'!$E$6:$E$19,"Diego")+COUNTIFS('S7'!$B$6:$B$19,$A45,'S7'!$E$6:$E$19,"Ambos")+COUNTIFS('S8'!$B$6:$B$23,$A45,'S8'!$E$6:$E$23,"Diego")+COUNTIFS('S8'!$B$6:$B$23,$A45,'S8'!$E$6:$E$23,"Ambos")+COUNTIFS('S9'!$B$6:$B$15,$A45,'S9'!$E$6:$E$15,"Diego")+COUNTIFS('S9'!$B$6:$B$15,$A45,'S9'!$E$6:$E$15,"Ambos")+COUNTIFS('S10'!$B$6:$B$13,$A45,'S10'!$E$6:$E$13,"Diego")+COUNTIFS('S10'!$B$6:$B$13,$A45,'S10'!$E$6:$E$13,"Ambos")+COUNTIFS('Holgura'!$B$6:$B$11,$A45,'Holgura'!$E$6:$E$11,"Diego")+COUNTIFS('Holgura'!$B$6:$B$11,$A45,'Holgura'!$E$6:$E$11,"Ambos")+COUNTIFS('Entrega'!$B$6:$B$9,$A45,'Entrega'!$E$6:$E$9,"Diego")+COUNTIFS('Entrega'!$B$6:$B$9,$A45,'Entrega'!$E$6:$E$9,"Ambos")+COUNTIFS('Defensa'!$B$6:$B$10,$A45,'Defensa'!$E$6:$E$10,"Diego")+COUNTIFS('Defensa'!$B$6:$B$10,$A45,'Defensa'!$E$6:$E$10,"Ambos")</f>
         <v/>
       </c>
     </row>
@@ -9869,19 +9890,19 @@
         <v/>
       </c>
       <c r="D46" s="21">
-        <f>SUMIFS('S1'!$I$6:$I$32,'S1'!$B$6:$B$32,$A46,'S1'!$E$6:$E$32,"Víctor")+SUMIFS('S1'!$I$6:$I$32,'S1'!$B$6:$B$32,$A46,'S1'!$E$6:$E$32,"Ambos")+SUMIFS('S2'!$I$6:$I$23,'S2'!$B$6:$B$23,$A46,'S2'!$E$6:$E$23,"Víctor")+SUMIFS('S2'!$I$6:$I$23,'S2'!$B$6:$B$23,$A46,'S2'!$E$6:$E$23,"Ambos")+SUMIFS('S3'!$I$6:$I$19,'S3'!$B$6:$B$19,$A46,'S3'!$E$6:$E$19,"Víctor")+SUMIFS('S3'!$I$6:$I$19,'S3'!$B$6:$B$19,$A46,'S3'!$E$6:$E$19,"Ambos")+SUMIFS('S4'!$I$6:$I$20,'S4'!$B$6:$B$20,$A46,'S4'!$E$6:$E$20,"Víctor")+SUMIFS('S4'!$I$6:$I$20,'S4'!$B$6:$B$20,$A46,'S4'!$E$6:$E$20,"Ambos")+SUMIFS('S5'!$I$6:$I$20,'S5'!$B$6:$B$20,$A46,'S5'!$E$6:$E$20,"Víctor")+SUMIFS('S5'!$I$6:$I$20,'S5'!$B$6:$B$20,$A46,'S5'!$E$6:$E$20,"Ambos")+SUMIFS('S6'!$I$6:$I$17,'S6'!$B$6:$B$17,$A46,'S6'!$E$6:$E$17,"Víctor")+SUMIFS('S6'!$I$6:$I$17,'S6'!$B$6:$B$17,$A46,'S6'!$E$6:$E$17,"Ambos")+SUMIFS('S7'!$I$6:$I$19,'S7'!$B$6:$B$19,$A46,'S7'!$E$6:$E$19,"Víctor")+SUMIFS('S7'!$I$6:$I$19,'S7'!$B$6:$B$19,$A46,'S7'!$E$6:$E$19,"Ambos")+SUMIFS('S8'!$I$6:$I$23,'S8'!$B$6:$B$23,$A46,'S8'!$E$6:$E$23,"Víctor")+SUMIFS('S8'!$I$6:$I$23,'S8'!$B$6:$B$23,$A46,'S8'!$E$6:$E$23,"Ambos")+SUMIFS('S9'!$I$6:$I$15,'S9'!$B$6:$B$15,$A46,'S9'!$E$6:$E$15,"Víctor")+SUMIFS('S9'!$I$6:$I$15,'S9'!$B$6:$B$15,$A46,'S9'!$E$6:$E$15,"Ambos")+SUMIFS('S10'!$I$6:$I$13,'S10'!$B$6:$B$13,$A46,'S10'!$E$6:$E$13,"Víctor")+SUMIFS('S10'!$I$6:$I$13,'S10'!$B$6:$B$13,$A46,'S10'!$E$6:$E$13,"Ambos")+SUMIFS('Holgura'!$I$6:$I$11,'Holgura'!$B$6:$B$11,$A46,'Holgura'!$E$6:$E$11,"Víctor")+SUMIFS('Holgura'!$I$6:$I$11,'Holgura'!$B$6:$B$11,$A46,'Holgura'!$E$6:$E$11,"Ambos")+SUMIFS('Entrega'!$I$6:$I$9,'Entrega'!$B$6:$B$9,$A46,'Entrega'!$E$6:$E$9,"Víctor")+SUMIFS('Entrega'!$I$6:$I$9,'Entrega'!$B$6:$B$9,$A46,'Entrega'!$E$6:$E$9,"Ambos")+SUMIFS('Defensa'!$I$6:$I$10,'Defensa'!$B$6:$B$10,$A46,'Defensa'!$E$6:$E$10,"Víctor")+SUMIFS('Defensa'!$I$6:$I$10,'Defensa'!$B$6:$B$10,$A46,'Defensa'!$E$6:$E$10,"Ambos")</f>
+        <f>SUMIFS('S1'!$I$6:$I$32,'S1'!$B$6:$B$32,$A46,'S1'!$E$6:$E$32,"Víctor")+SUMIFS('S1'!$I$6:$I$32,'S1'!$B$6:$B$32,$A46,'S1'!$E$6:$E$32,"Ambos")+SUMIFS('S2'!$I$6:$I$23,'S2'!$B$6:$B$23,$A46,'S2'!$E$6:$E$23,"Víctor")+SUMIFS('S2'!$I$6:$I$23,'S2'!$B$6:$B$23,$A46,'S2'!$E$6:$E$23,"Ambos")+SUMIFS('S3'!$I$6:$I$24,'S3'!$B$6:$B$24,$A46,'S3'!$E$6:$E$24,"Víctor")+SUMIFS('S3'!$I$6:$I$24,'S3'!$B$6:$B$24,$A46,'S3'!$E$6:$E$24,"Ambos")+SUMIFS('S4'!$I$6:$I$22,'S4'!$B$6:$B$22,$A46,'S4'!$E$6:$E$22,"Víctor")+SUMIFS('S4'!$I$6:$I$22,'S4'!$B$6:$B$22,$A46,'S4'!$E$6:$E$22,"Ambos")+SUMIFS('S5'!$I$6:$I$20,'S5'!$B$6:$B$20,$A46,'S5'!$E$6:$E$20,"Víctor")+SUMIFS('S5'!$I$6:$I$20,'S5'!$B$6:$B$20,$A46,'S5'!$E$6:$E$20,"Ambos")+SUMIFS('S6'!$I$6:$I$17,'S6'!$B$6:$B$17,$A46,'S6'!$E$6:$E$17,"Víctor")+SUMIFS('S6'!$I$6:$I$17,'S6'!$B$6:$B$17,$A46,'S6'!$E$6:$E$17,"Ambos")+SUMIFS('S7'!$I$6:$I$19,'S7'!$B$6:$B$19,$A46,'S7'!$E$6:$E$19,"Víctor")+SUMIFS('S7'!$I$6:$I$19,'S7'!$B$6:$B$19,$A46,'S7'!$E$6:$E$19,"Ambos")+SUMIFS('S8'!$I$6:$I$23,'S8'!$B$6:$B$23,$A46,'S8'!$E$6:$E$23,"Víctor")+SUMIFS('S8'!$I$6:$I$23,'S8'!$B$6:$B$23,$A46,'S8'!$E$6:$E$23,"Ambos")+SUMIFS('S9'!$I$6:$I$15,'S9'!$B$6:$B$15,$A46,'S9'!$E$6:$E$15,"Víctor")+SUMIFS('S9'!$I$6:$I$15,'S9'!$B$6:$B$15,$A46,'S9'!$E$6:$E$15,"Ambos")+SUMIFS('S10'!$I$6:$I$13,'S10'!$B$6:$B$13,$A46,'S10'!$E$6:$E$13,"Víctor")+SUMIFS('S10'!$I$6:$I$13,'S10'!$B$6:$B$13,$A46,'S10'!$E$6:$E$13,"Ambos")+SUMIFS('Holgura'!$I$6:$I$11,'Holgura'!$B$6:$B$11,$A46,'Holgura'!$E$6:$E$11,"Víctor")+SUMIFS('Holgura'!$I$6:$I$11,'Holgura'!$B$6:$B$11,$A46,'Holgura'!$E$6:$E$11,"Ambos")+SUMIFS('Entrega'!$I$6:$I$9,'Entrega'!$B$6:$B$9,$A46,'Entrega'!$E$6:$E$9,"Víctor")+SUMIFS('Entrega'!$I$6:$I$9,'Entrega'!$B$6:$B$9,$A46,'Entrega'!$E$6:$E$9,"Ambos")+SUMIFS('Defensa'!$I$6:$I$10,'Defensa'!$B$6:$B$10,$A46,'Defensa'!$E$6:$E$10,"Víctor")+SUMIFS('Defensa'!$I$6:$I$10,'Defensa'!$B$6:$B$10,$A46,'Defensa'!$E$6:$E$10,"Ambos")</f>
         <v/>
       </c>
       <c r="E46" s="21">
-        <f>SUMIFS('S1'!$I$6:$I$32,'S1'!$B$6:$B$32,$A46,'S1'!$E$6:$E$32,"Diego")+SUMIFS('S1'!$I$6:$I$32,'S1'!$B$6:$B$32,$A46,'S1'!$E$6:$E$32,"Ambos")+SUMIFS('S2'!$I$6:$I$23,'S2'!$B$6:$B$23,$A46,'S2'!$E$6:$E$23,"Diego")+SUMIFS('S2'!$I$6:$I$23,'S2'!$B$6:$B$23,$A46,'S2'!$E$6:$E$23,"Ambos")+SUMIFS('S3'!$I$6:$I$19,'S3'!$B$6:$B$19,$A46,'S3'!$E$6:$E$19,"Diego")+SUMIFS('S3'!$I$6:$I$19,'S3'!$B$6:$B$19,$A46,'S3'!$E$6:$E$19,"Ambos")+SUMIFS('S4'!$I$6:$I$20,'S4'!$B$6:$B$20,$A46,'S4'!$E$6:$E$20,"Diego")+SUMIFS('S4'!$I$6:$I$20,'S4'!$B$6:$B$20,$A46,'S4'!$E$6:$E$20,"Ambos")+SUMIFS('S5'!$I$6:$I$20,'S5'!$B$6:$B$20,$A46,'S5'!$E$6:$E$20,"Diego")+SUMIFS('S5'!$I$6:$I$20,'S5'!$B$6:$B$20,$A46,'S5'!$E$6:$E$20,"Ambos")+SUMIFS('S6'!$I$6:$I$17,'S6'!$B$6:$B$17,$A46,'S6'!$E$6:$E$17,"Diego")+SUMIFS('S6'!$I$6:$I$17,'S6'!$B$6:$B$17,$A46,'S6'!$E$6:$E$17,"Ambos")+SUMIFS('S7'!$I$6:$I$19,'S7'!$B$6:$B$19,$A46,'S7'!$E$6:$E$19,"Diego")+SUMIFS('S7'!$I$6:$I$19,'S7'!$B$6:$B$19,$A46,'S7'!$E$6:$E$19,"Ambos")+SUMIFS('S8'!$I$6:$I$23,'S8'!$B$6:$B$23,$A46,'S8'!$E$6:$E$23,"Diego")+SUMIFS('S8'!$I$6:$I$23,'S8'!$B$6:$B$23,$A46,'S8'!$E$6:$E$23,"Ambos")+SUMIFS('S9'!$I$6:$I$15,'S9'!$B$6:$B$15,$A46,'S9'!$E$6:$E$15,"Diego")+SUMIFS('S9'!$I$6:$I$15,'S9'!$B$6:$B$15,$A46,'S9'!$E$6:$E$15,"Ambos")+SUMIFS('S10'!$I$6:$I$13,'S10'!$B$6:$B$13,$A46,'S10'!$E$6:$E$13,"Diego")+SUMIFS('S10'!$I$6:$I$13,'S10'!$B$6:$B$13,$A46,'S10'!$E$6:$E$13,"Ambos")+SUMIFS('Holgura'!$I$6:$I$11,'Holgura'!$B$6:$B$11,$A46,'Holgura'!$E$6:$E$11,"Diego")+SUMIFS('Holgura'!$I$6:$I$11,'Holgura'!$B$6:$B$11,$A46,'Holgura'!$E$6:$E$11,"Ambos")+SUMIFS('Entrega'!$I$6:$I$9,'Entrega'!$B$6:$B$9,$A46,'Entrega'!$E$6:$E$9,"Diego")+SUMIFS('Entrega'!$I$6:$I$9,'Entrega'!$B$6:$B$9,$A46,'Entrega'!$E$6:$E$9,"Ambos")+SUMIFS('Defensa'!$I$6:$I$10,'Defensa'!$B$6:$B$10,$A46,'Defensa'!$E$6:$E$10,"Diego")+SUMIFS('Defensa'!$I$6:$I$10,'Defensa'!$B$6:$B$10,$A46,'Defensa'!$E$6:$E$10,"Ambos")</f>
+        <f>SUMIFS('S1'!$I$6:$I$32,'S1'!$B$6:$B$32,$A46,'S1'!$E$6:$E$32,"Diego")+SUMIFS('S1'!$I$6:$I$32,'S1'!$B$6:$B$32,$A46,'S1'!$E$6:$E$32,"Ambos")+SUMIFS('S2'!$I$6:$I$23,'S2'!$B$6:$B$23,$A46,'S2'!$E$6:$E$23,"Diego")+SUMIFS('S2'!$I$6:$I$23,'S2'!$B$6:$B$23,$A46,'S2'!$E$6:$E$23,"Ambos")+SUMIFS('S3'!$I$6:$I$24,'S3'!$B$6:$B$24,$A46,'S3'!$E$6:$E$24,"Diego")+SUMIFS('S3'!$I$6:$I$24,'S3'!$B$6:$B$24,$A46,'S3'!$E$6:$E$24,"Ambos")+SUMIFS('S4'!$I$6:$I$22,'S4'!$B$6:$B$22,$A46,'S4'!$E$6:$E$22,"Diego")+SUMIFS('S4'!$I$6:$I$22,'S4'!$B$6:$B$22,$A46,'S4'!$E$6:$E$22,"Ambos")+SUMIFS('S5'!$I$6:$I$20,'S5'!$B$6:$B$20,$A46,'S5'!$E$6:$E$20,"Diego")+SUMIFS('S5'!$I$6:$I$20,'S5'!$B$6:$B$20,$A46,'S5'!$E$6:$E$20,"Ambos")+SUMIFS('S6'!$I$6:$I$17,'S6'!$B$6:$B$17,$A46,'S6'!$E$6:$E$17,"Diego")+SUMIFS('S6'!$I$6:$I$17,'S6'!$B$6:$B$17,$A46,'S6'!$E$6:$E$17,"Ambos")+SUMIFS('S7'!$I$6:$I$19,'S7'!$B$6:$B$19,$A46,'S7'!$E$6:$E$19,"Diego")+SUMIFS('S7'!$I$6:$I$19,'S7'!$B$6:$B$19,$A46,'S7'!$E$6:$E$19,"Ambos")+SUMIFS('S8'!$I$6:$I$23,'S8'!$B$6:$B$23,$A46,'S8'!$E$6:$E$23,"Diego")+SUMIFS('S8'!$I$6:$I$23,'S8'!$B$6:$B$23,$A46,'S8'!$E$6:$E$23,"Ambos")+SUMIFS('S9'!$I$6:$I$15,'S9'!$B$6:$B$15,$A46,'S9'!$E$6:$E$15,"Diego")+SUMIFS('S9'!$I$6:$I$15,'S9'!$B$6:$B$15,$A46,'S9'!$E$6:$E$15,"Ambos")+SUMIFS('S10'!$I$6:$I$13,'S10'!$B$6:$B$13,$A46,'S10'!$E$6:$E$13,"Diego")+SUMIFS('S10'!$I$6:$I$13,'S10'!$B$6:$B$13,$A46,'S10'!$E$6:$E$13,"Ambos")+SUMIFS('Holgura'!$I$6:$I$11,'Holgura'!$B$6:$B$11,$A46,'Holgura'!$E$6:$E$11,"Diego")+SUMIFS('Holgura'!$I$6:$I$11,'Holgura'!$B$6:$B$11,$A46,'Holgura'!$E$6:$E$11,"Ambos")+SUMIFS('Entrega'!$I$6:$I$9,'Entrega'!$B$6:$B$9,$A46,'Entrega'!$E$6:$E$9,"Diego")+SUMIFS('Entrega'!$I$6:$I$9,'Entrega'!$B$6:$B$9,$A46,'Entrega'!$E$6:$E$9,"Ambos")+SUMIFS('Defensa'!$I$6:$I$10,'Defensa'!$B$6:$B$10,$A46,'Defensa'!$E$6:$E$10,"Diego")+SUMIFS('Defensa'!$I$6:$I$10,'Defensa'!$B$6:$B$10,$A46,'Defensa'!$E$6:$E$10,"Ambos")</f>
         <v/>
       </c>
       <c r="F46" s="21">
-        <f>COUNTIFS('S1'!$B$6:$B$32,$A46,'S1'!$E$6:$E$32,"Víctor")+COUNTIFS('S1'!$B$6:$B$32,$A46,'S1'!$E$6:$E$32,"Ambos")+COUNTIFS('S2'!$B$6:$B$23,$A46,'S2'!$E$6:$E$23,"Víctor")+COUNTIFS('S2'!$B$6:$B$23,$A46,'S2'!$E$6:$E$23,"Ambos")+COUNTIFS('S3'!$B$6:$B$19,$A46,'S3'!$E$6:$E$19,"Víctor")+COUNTIFS('S3'!$B$6:$B$19,$A46,'S3'!$E$6:$E$19,"Ambos")+COUNTIFS('S4'!$B$6:$B$20,$A46,'S4'!$E$6:$E$20,"Víctor")+COUNTIFS('S4'!$B$6:$B$20,$A46,'S4'!$E$6:$E$20,"Ambos")+COUNTIFS('S5'!$B$6:$B$20,$A46,'S5'!$E$6:$E$20,"Víctor")+COUNTIFS('S5'!$B$6:$B$20,$A46,'S5'!$E$6:$E$20,"Ambos")+COUNTIFS('S6'!$B$6:$B$17,$A46,'S6'!$E$6:$E$17,"Víctor")+COUNTIFS('S6'!$B$6:$B$17,$A46,'S6'!$E$6:$E$17,"Ambos")+COUNTIFS('S7'!$B$6:$B$19,$A46,'S7'!$E$6:$E$19,"Víctor")+COUNTIFS('S7'!$B$6:$B$19,$A46,'S7'!$E$6:$E$19,"Ambos")+COUNTIFS('S8'!$B$6:$B$23,$A46,'S8'!$E$6:$E$23,"Víctor")+COUNTIFS('S8'!$B$6:$B$23,$A46,'S8'!$E$6:$E$23,"Ambos")+COUNTIFS('S9'!$B$6:$B$15,$A46,'S9'!$E$6:$E$15,"Víctor")+COUNTIFS('S9'!$B$6:$B$15,$A46,'S9'!$E$6:$E$15,"Ambos")+COUNTIFS('S10'!$B$6:$B$13,$A46,'S10'!$E$6:$E$13,"Víctor")+COUNTIFS('S10'!$B$6:$B$13,$A46,'S10'!$E$6:$E$13,"Ambos")+COUNTIFS('Holgura'!$B$6:$B$11,$A46,'Holgura'!$E$6:$E$11,"Víctor")+COUNTIFS('Holgura'!$B$6:$B$11,$A46,'Holgura'!$E$6:$E$11,"Ambos")+COUNTIFS('Entrega'!$B$6:$B$9,$A46,'Entrega'!$E$6:$E$9,"Víctor")+COUNTIFS('Entrega'!$B$6:$B$9,$A46,'Entrega'!$E$6:$E$9,"Ambos")+COUNTIFS('Defensa'!$B$6:$B$10,$A46,'Defensa'!$E$6:$E$10,"Víctor")+COUNTIFS('Defensa'!$B$6:$B$10,$A46,'Defensa'!$E$6:$E$10,"Ambos")</f>
+        <f>COUNTIFS('S1'!$B$6:$B$32,$A46,'S1'!$E$6:$E$32,"Víctor")+COUNTIFS('S1'!$B$6:$B$32,$A46,'S1'!$E$6:$E$32,"Ambos")+COUNTIFS('S2'!$B$6:$B$23,$A46,'S2'!$E$6:$E$23,"Víctor")+COUNTIFS('S2'!$B$6:$B$23,$A46,'S2'!$E$6:$E$23,"Ambos")+COUNTIFS('S3'!$B$6:$B$24,$A46,'S3'!$E$6:$E$24,"Víctor")+COUNTIFS('S3'!$B$6:$B$24,$A46,'S3'!$E$6:$E$24,"Ambos")+COUNTIFS('S4'!$B$6:$B$22,$A46,'S4'!$E$6:$E$22,"Víctor")+COUNTIFS('S4'!$B$6:$B$22,$A46,'S4'!$E$6:$E$22,"Ambos")+COUNTIFS('S5'!$B$6:$B$20,$A46,'S5'!$E$6:$E$20,"Víctor")+COUNTIFS('S5'!$B$6:$B$20,$A46,'S5'!$E$6:$E$20,"Ambos")+COUNTIFS('S6'!$B$6:$B$17,$A46,'S6'!$E$6:$E$17,"Víctor")+COUNTIFS('S6'!$B$6:$B$17,$A46,'S6'!$E$6:$E$17,"Ambos")+COUNTIFS('S7'!$B$6:$B$19,$A46,'S7'!$E$6:$E$19,"Víctor")+COUNTIFS('S7'!$B$6:$B$19,$A46,'S7'!$E$6:$E$19,"Ambos")+COUNTIFS('S8'!$B$6:$B$23,$A46,'S8'!$E$6:$E$23,"Víctor")+COUNTIFS('S8'!$B$6:$B$23,$A46,'S8'!$E$6:$E$23,"Ambos")+COUNTIFS('S9'!$B$6:$B$15,$A46,'S9'!$E$6:$E$15,"Víctor")+COUNTIFS('S9'!$B$6:$B$15,$A46,'S9'!$E$6:$E$15,"Ambos")+COUNTIFS('S10'!$B$6:$B$13,$A46,'S10'!$E$6:$E$13,"Víctor")+COUNTIFS('S10'!$B$6:$B$13,$A46,'S10'!$E$6:$E$13,"Ambos")+COUNTIFS('Holgura'!$B$6:$B$11,$A46,'Holgura'!$E$6:$E$11,"Víctor")+COUNTIFS('Holgura'!$B$6:$B$11,$A46,'Holgura'!$E$6:$E$11,"Ambos")+COUNTIFS('Entrega'!$B$6:$B$9,$A46,'Entrega'!$E$6:$E$9,"Víctor")+COUNTIFS('Entrega'!$B$6:$B$9,$A46,'Entrega'!$E$6:$E$9,"Ambos")+COUNTIFS('Defensa'!$B$6:$B$10,$A46,'Defensa'!$E$6:$E$10,"Víctor")+COUNTIFS('Defensa'!$B$6:$B$10,$A46,'Defensa'!$E$6:$E$10,"Ambos")</f>
         <v/>
       </c>
       <c r="G46" s="21">
-        <f>COUNTIFS('S1'!$B$6:$B$32,$A46,'S1'!$E$6:$E$32,"Diego")+COUNTIFS('S1'!$B$6:$B$32,$A46,'S1'!$E$6:$E$32,"Ambos")+COUNTIFS('S2'!$B$6:$B$23,$A46,'S2'!$E$6:$E$23,"Diego")+COUNTIFS('S2'!$B$6:$B$23,$A46,'S2'!$E$6:$E$23,"Ambos")+COUNTIFS('S3'!$B$6:$B$19,$A46,'S3'!$E$6:$E$19,"Diego")+COUNTIFS('S3'!$B$6:$B$19,$A46,'S3'!$E$6:$E$19,"Ambos")+COUNTIFS('S4'!$B$6:$B$20,$A46,'S4'!$E$6:$E$20,"Diego")+COUNTIFS('S4'!$B$6:$B$20,$A46,'S4'!$E$6:$E$20,"Ambos")+COUNTIFS('S5'!$B$6:$B$20,$A46,'S5'!$E$6:$E$20,"Diego")+COUNTIFS('S5'!$B$6:$B$20,$A46,'S5'!$E$6:$E$20,"Ambos")+COUNTIFS('S6'!$B$6:$B$17,$A46,'S6'!$E$6:$E$17,"Diego")+COUNTIFS('S6'!$B$6:$B$17,$A46,'S6'!$E$6:$E$17,"Ambos")+COUNTIFS('S7'!$B$6:$B$19,$A46,'S7'!$E$6:$E$19,"Diego")+COUNTIFS('S7'!$B$6:$B$19,$A46,'S7'!$E$6:$E$19,"Ambos")+COUNTIFS('S8'!$B$6:$B$23,$A46,'S8'!$E$6:$E$23,"Diego")+COUNTIFS('S8'!$B$6:$B$23,$A46,'S8'!$E$6:$E$23,"Ambos")+COUNTIFS('S9'!$B$6:$B$15,$A46,'S9'!$E$6:$E$15,"Diego")+COUNTIFS('S9'!$B$6:$B$15,$A46,'S9'!$E$6:$E$15,"Ambos")+COUNTIFS('S10'!$B$6:$B$13,$A46,'S10'!$E$6:$E$13,"Diego")+COUNTIFS('S10'!$B$6:$B$13,$A46,'S10'!$E$6:$E$13,"Ambos")+COUNTIFS('Holgura'!$B$6:$B$11,$A46,'Holgura'!$E$6:$E$11,"Diego")+COUNTIFS('Holgura'!$B$6:$B$11,$A46,'Holgura'!$E$6:$E$11,"Ambos")+COUNTIFS('Entrega'!$B$6:$B$9,$A46,'Entrega'!$E$6:$E$9,"Diego")+COUNTIFS('Entrega'!$B$6:$B$9,$A46,'Entrega'!$E$6:$E$9,"Ambos")+COUNTIFS('Defensa'!$B$6:$B$10,$A46,'Defensa'!$E$6:$E$10,"Diego")+COUNTIFS('Defensa'!$B$6:$B$10,$A46,'Defensa'!$E$6:$E$10,"Ambos")</f>
+        <f>COUNTIFS('S1'!$B$6:$B$32,$A46,'S1'!$E$6:$E$32,"Diego")+COUNTIFS('S1'!$B$6:$B$32,$A46,'S1'!$E$6:$E$32,"Ambos")+COUNTIFS('S2'!$B$6:$B$23,$A46,'S2'!$E$6:$E$23,"Diego")+COUNTIFS('S2'!$B$6:$B$23,$A46,'S2'!$E$6:$E$23,"Ambos")+COUNTIFS('S3'!$B$6:$B$24,$A46,'S3'!$E$6:$E$24,"Diego")+COUNTIFS('S3'!$B$6:$B$24,$A46,'S3'!$E$6:$E$24,"Ambos")+COUNTIFS('S4'!$B$6:$B$22,$A46,'S4'!$E$6:$E$22,"Diego")+COUNTIFS('S4'!$B$6:$B$22,$A46,'S4'!$E$6:$E$22,"Ambos")+COUNTIFS('S5'!$B$6:$B$20,$A46,'S5'!$E$6:$E$20,"Diego")+COUNTIFS('S5'!$B$6:$B$20,$A46,'S5'!$E$6:$E$20,"Ambos")+COUNTIFS('S6'!$B$6:$B$17,$A46,'S6'!$E$6:$E$17,"Diego")+COUNTIFS('S6'!$B$6:$B$17,$A46,'S6'!$E$6:$E$17,"Ambos")+COUNTIFS('S7'!$B$6:$B$19,$A46,'S7'!$E$6:$E$19,"Diego")+COUNTIFS('S7'!$B$6:$B$19,$A46,'S7'!$E$6:$E$19,"Ambos")+COUNTIFS('S8'!$B$6:$B$23,$A46,'S8'!$E$6:$E$23,"Diego")+COUNTIFS('S8'!$B$6:$B$23,$A46,'S8'!$E$6:$E$23,"Ambos")+COUNTIFS('S9'!$B$6:$B$15,$A46,'S9'!$E$6:$E$15,"Diego")+COUNTIFS('S9'!$B$6:$B$15,$A46,'S9'!$E$6:$E$15,"Ambos")+COUNTIFS('S10'!$B$6:$B$13,$A46,'S10'!$E$6:$E$13,"Diego")+COUNTIFS('S10'!$B$6:$B$13,$A46,'S10'!$E$6:$E$13,"Ambos")+COUNTIFS('Holgura'!$B$6:$B$11,$A46,'Holgura'!$E$6:$E$11,"Diego")+COUNTIFS('Holgura'!$B$6:$B$11,$A46,'Holgura'!$E$6:$E$11,"Ambos")+COUNTIFS('Entrega'!$B$6:$B$9,$A46,'Entrega'!$E$6:$E$9,"Diego")+COUNTIFS('Entrega'!$B$6:$B$9,$A46,'Entrega'!$E$6:$E$9,"Ambos")+COUNTIFS('Defensa'!$B$6:$B$10,$A46,'Defensa'!$E$6:$E$10,"Diego")+COUNTIFS('Defensa'!$B$6:$B$10,$A46,'Defensa'!$E$6:$E$10,"Ambos")</f>
         <v/>
       </c>
     </row>
@@ -9898,19 +9919,19 @@
         <v/>
       </c>
       <c r="D47" s="21">
-        <f>SUMIFS('S1'!$I$6:$I$32,'S1'!$B$6:$B$32,$A47,'S1'!$E$6:$E$32,"Víctor")+SUMIFS('S1'!$I$6:$I$32,'S1'!$B$6:$B$32,$A47,'S1'!$E$6:$E$32,"Ambos")+SUMIFS('S2'!$I$6:$I$23,'S2'!$B$6:$B$23,$A47,'S2'!$E$6:$E$23,"Víctor")+SUMIFS('S2'!$I$6:$I$23,'S2'!$B$6:$B$23,$A47,'S2'!$E$6:$E$23,"Ambos")+SUMIFS('S3'!$I$6:$I$19,'S3'!$B$6:$B$19,$A47,'S3'!$E$6:$E$19,"Víctor")+SUMIFS('S3'!$I$6:$I$19,'S3'!$B$6:$B$19,$A47,'S3'!$E$6:$E$19,"Ambos")+SUMIFS('S4'!$I$6:$I$20,'S4'!$B$6:$B$20,$A47,'S4'!$E$6:$E$20,"Víctor")+SUMIFS('S4'!$I$6:$I$20,'S4'!$B$6:$B$20,$A47,'S4'!$E$6:$E$20,"Ambos")+SUMIFS('S5'!$I$6:$I$20,'S5'!$B$6:$B$20,$A47,'S5'!$E$6:$E$20,"Víctor")+SUMIFS('S5'!$I$6:$I$20,'S5'!$B$6:$B$20,$A47,'S5'!$E$6:$E$20,"Ambos")+SUMIFS('S6'!$I$6:$I$17,'S6'!$B$6:$B$17,$A47,'S6'!$E$6:$E$17,"Víctor")+SUMIFS('S6'!$I$6:$I$17,'S6'!$B$6:$B$17,$A47,'S6'!$E$6:$E$17,"Ambos")+SUMIFS('S7'!$I$6:$I$19,'S7'!$B$6:$B$19,$A47,'S7'!$E$6:$E$19,"Víctor")+SUMIFS('S7'!$I$6:$I$19,'S7'!$B$6:$B$19,$A47,'S7'!$E$6:$E$19,"Ambos")+SUMIFS('S8'!$I$6:$I$23,'S8'!$B$6:$B$23,$A47,'S8'!$E$6:$E$23,"Víctor")+SUMIFS('S8'!$I$6:$I$23,'S8'!$B$6:$B$23,$A47,'S8'!$E$6:$E$23,"Ambos")+SUMIFS('S9'!$I$6:$I$15,'S9'!$B$6:$B$15,$A47,'S9'!$E$6:$E$15,"Víctor")+SUMIFS('S9'!$I$6:$I$15,'S9'!$B$6:$B$15,$A47,'S9'!$E$6:$E$15,"Ambos")+SUMIFS('S10'!$I$6:$I$13,'S10'!$B$6:$B$13,$A47,'S10'!$E$6:$E$13,"Víctor")+SUMIFS('S10'!$I$6:$I$13,'S10'!$B$6:$B$13,$A47,'S10'!$E$6:$E$13,"Ambos")+SUMIFS('Holgura'!$I$6:$I$11,'Holgura'!$B$6:$B$11,$A47,'Holgura'!$E$6:$E$11,"Víctor")+SUMIFS('Holgura'!$I$6:$I$11,'Holgura'!$B$6:$B$11,$A47,'Holgura'!$E$6:$E$11,"Ambos")+SUMIFS('Entrega'!$I$6:$I$9,'Entrega'!$B$6:$B$9,$A47,'Entrega'!$E$6:$E$9,"Víctor")+SUMIFS('Entrega'!$I$6:$I$9,'Entrega'!$B$6:$B$9,$A47,'Entrega'!$E$6:$E$9,"Ambos")+SUMIFS('Defensa'!$I$6:$I$10,'Defensa'!$B$6:$B$10,$A47,'Defensa'!$E$6:$E$10,"Víctor")+SUMIFS('Defensa'!$I$6:$I$10,'Defensa'!$B$6:$B$10,$A47,'Defensa'!$E$6:$E$10,"Ambos")</f>
+        <f>SUMIFS('S1'!$I$6:$I$32,'S1'!$B$6:$B$32,$A47,'S1'!$E$6:$E$32,"Víctor")+SUMIFS('S1'!$I$6:$I$32,'S1'!$B$6:$B$32,$A47,'S1'!$E$6:$E$32,"Ambos")+SUMIFS('S2'!$I$6:$I$23,'S2'!$B$6:$B$23,$A47,'S2'!$E$6:$E$23,"Víctor")+SUMIFS('S2'!$I$6:$I$23,'S2'!$B$6:$B$23,$A47,'S2'!$E$6:$E$23,"Ambos")+SUMIFS('S3'!$I$6:$I$24,'S3'!$B$6:$B$24,$A47,'S3'!$E$6:$E$24,"Víctor")+SUMIFS('S3'!$I$6:$I$24,'S3'!$B$6:$B$24,$A47,'S3'!$E$6:$E$24,"Ambos")+SUMIFS('S4'!$I$6:$I$22,'S4'!$B$6:$B$22,$A47,'S4'!$E$6:$E$22,"Víctor")+SUMIFS('S4'!$I$6:$I$22,'S4'!$B$6:$B$22,$A47,'S4'!$E$6:$E$22,"Ambos")+SUMIFS('S5'!$I$6:$I$20,'S5'!$B$6:$B$20,$A47,'S5'!$E$6:$E$20,"Víctor")+SUMIFS('S5'!$I$6:$I$20,'S5'!$B$6:$B$20,$A47,'S5'!$E$6:$E$20,"Ambos")+SUMIFS('S6'!$I$6:$I$17,'S6'!$B$6:$B$17,$A47,'S6'!$E$6:$E$17,"Víctor")+SUMIFS('S6'!$I$6:$I$17,'S6'!$B$6:$B$17,$A47,'S6'!$E$6:$E$17,"Ambos")+SUMIFS('S7'!$I$6:$I$19,'S7'!$B$6:$B$19,$A47,'S7'!$E$6:$E$19,"Víctor")+SUMIFS('S7'!$I$6:$I$19,'S7'!$B$6:$B$19,$A47,'S7'!$E$6:$E$19,"Ambos")+SUMIFS('S8'!$I$6:$I$23,'S8'!$B$6:$B$23,$A47,'S8'!$E$6:$E$23,"Víctor")+SUMIFS('S8'!$I$6:$I$23,'S8'!$B$6:$B$23,$A47,'S8'!$E$6:$E$23,"Ambos")+SUMIFS('S9'!$I$6:$I$15,'S9'!$B$6:$B$15,$A47,'S9'!$E$6:$E$15,"Víctor")+SUMIFS('S9'!$I$6:$I$15,'S9'!$B$6:$B$15,$A47,'S9'!$E$6:$E$15,"Ambos")+SUMIFS('S10'!$I$6:$I$13,'S10'!$B$6:$B$13,$A47,'S10'!$E$6:$E$13,"Víctor")+SUMIFS('S10'!$I$6:$I$13,'S10'!$B$6:$B$13,$A47,'S10'!$E$6:$E$13,"Ambos")+SUMIFS('Holgura'!$I$6:$I$11,'Holgura'!$B$6:$B$11,$A47,'Holgura'!$E$6:$E$11,"Víctor")+SUMIFS('Holgura'!$I$6:$I$11,'Holgura'!$B$6:$B$11,$A47,'Holgura'!$E$6:$E$11,"Ambos")+SUMIFS('Entrega'!$I$6:$I$9,'Entrega'!$B$6:$B$9,$A47,'Entrega'!$E$6:$E$9,"Víctor")+SUMIFS('Entrega'!$I$6:$I$9,'Entrega'!$B$6:$B$9,$A47,'Entrega'!$E$6:$E$9,"Ambos")+SUMIFS('Defensa'!$I$6:$I$10,'Defensa'!$B$6:$B$10,$A47,'Defensa'!$E$6:$E$10,"Víctor")+SUMIFS('Defensa'!$I$6:$I$10,'Defensa'!$B$6:$B$10,$A47,'Defensa'!$E$6:$E$10,"Ambos")</f>
         <v/>
       </c>
       <c r="E47" s="21">
-        <f>SUMIFS('S1'!$I$6:$I$32,'S1'!$B$6:$B$32,$A47,'S1'!$E$6:$E$32,"Diego")+SUMIFS('S1'!$I$6:$I$32,'S1'!$B$6:$B$32,$A47,'S1'!$E$6:$E$32,"Ambos")+SUMIFS('S2'!$I$6:$I$23,'S2'!$B$6:$B$23,$A47,'S2'!$E$6:$E$23,"Diego")+SUMIFS('S2'!$I$6:$I$23,'S2'!$B$6:$B$23,$A47,'S2'!$E$6:$E$23,"Ambos")+SUMIFS('S3'!$I$6:$I$19,'S3'!$B$6:$B$19,$A47,'S3'!$E$6:$E$19,"Diego")+SUMIFS('S3'!$I$6:$I$19,'S3'!$B$6:$B$19,$A47,'S3'!$E$6:$E$19,"Ambos")+SUMIFS('S4'!$I$6:$I$20,'S4'!$B$6:$B$20,$A47,'S4'!$E$6:$E$20,"Diego")+SUMIFS('S4'!$I$6:$I$20,'S4'!$B$6:$B$20,$A47,'S4'!$E$6:$E$20,"Ambos")+SUMIFS('S5'!$I$6:$I$20,'S5'!$B$6:$B$20,$A47,'S5'!$E$6:$E$20,"Diego")+SUMIFS('S5'!$I$6:$I$20,'S5'!$B$6:$B$20,$A47,'S5'!$E$6:$E$20,"Ambos")+SUMIFS('S6'!$I$6:$I$17,'S6'!$B$6:$B$17,$A47,'S6'!$E$6:$E$17,"Diego")+SUMIFS('S6'!$I$6:$I$17,'S6'!$B$6:$B$17,$A47,'S6'!$E$6:$E$17,"Ambos")+SUMIFS('S7'!$I$6:$I$19,'S7'!$B$6:$B$19,$A47,'S7'!$E$6:$E$19,"Diego")+SUMIFS('S7'!$I$6:$I$19,'S7'!$B$6:$B$19,$A47,'S7'!$E$6:$E$19,"Ambos")+SUMIFS('S8'!$I$6:$I$23,'S8'!$B$6:$B$23,$A47,'S8'!$E$6:$E$23,"Diego")+SUMIFS('S8'!$I$6:$I$23,'S8'!$B$6:$B$23,$A47,'S8'!$E$6:$E$23,"Ambos")+SUMIFS('S9'!$I$6:$I$15,'S9'!$B$6:$B$15,$A47,'S9'!$E$6:$E$15,"Diego")+SUMIFS('S9'!$I$6:$I$15,'S9'!$B$6:$B$15,$A47,'S9'!$E$6:$E$15,"Ambos")+SUMIFS('S10'!$I$6:$I$13,'S10'!$B$6:$B$13,$A47,'S10'!$E$6:$E$13,"Diego")+SUMIFS('S10'!$I$6:$I$13,'S10'!$B$6:$B$13,$A47,'S10'!$E$6:$E$13,"Ambos")+SUMIFS('Holgura'!$I$6:$I$11,'Holgura'!$B$6:$B$11,$A47,'Holgura'!$E$6:$E$11,"Diego")+SUMIFS('Holgura'!$I$6:$I$11,'Holgura'!$B$6:$B$11,$A47,'Holgura'!$E$6:$E$11,"Ambos")+SUMIFS('Entrega'!$I$6:$I$9,'Entrega'!$B$6:$B$9,$A47,'Entrega'!$E$6:$E$9,"Diego")+SUMIFS('Entrega'!$I$6:$I$9,'Entrega'!$B$6:$B$9,$A47,'Entrega'!$E$6:$E$9,"Ambos")+SUMIFS('Defensa'!$I$6:$I$10,'Defensa'!$B$6:$B$10,$A47,'Defensa'!$E$6:$E$10,"Diego")+SUMIFS('Defensa'!$I$6:$I$10,'Defensa'!$B$6:$B$10,$A47,'Defensa'!$E$6:$E$10,"Ambos")</f>
+        <f>SUMIFS('S1'!$I$6:$I$32,'S1'!$B$6:$B$32,$A47,'S1'!$E$6:$E$32,"Diego")+SUMIFS('S1'!$I$6:$I$32,'S1'!$B$6:$B$32,$A47,'S1'!$E$6:$E$32,"Ambos")+SUMIFS('S2'!$I$6:$I$23,'S2'!$B$6:$B$23,$A47,'S2'!$E$6:$E$23,"Diego")+SUMIFS('S2'!$I$6:$I$23,'S2'!$B$6:$B$23,$A47,'S2'!$E$6:$E$23,"Ambos")+SUMIFS('S3'!$I$6:$I$24,'S3'!$B$6:$B$24,$A47,'S3'!$E$6:$E$24,"Diego")+SUMIFS('S3'!$I$6:$I$24,'S3'!$B$6:$B$24,$A47,'S3'!$E$6:$E$24,"Ambos")+SUMIFS('S4'!$I$6:$I$22,'S4'!$B$6:$B$22,$A47,'S4'!$E$6:$E$22,"Diego")+SUMIFS('S4'!$I$6:$I$22,'S4'!$B$6:$B$22,$A47,'S4'!$E$6:$E$22,"Ambos")+SUMIFS('S5'!$I$6:$I$20,'S5'!$B$6:$B$20,$A47,'S5'!$E$6:$E$20,"Diego")+SUMIFS('S5'!$I$6:$I$20,'S5'!$B$6:$B$20,$A47,'S5'!$E$6:$E$20,"Ambos")+SUMIFS('S6'!$I$6:$I$17,'S6'!$B$6:$B$17,$A47,'S6'!$E$6:$E$17,"Diego")+SUMIFS('S6'!$I$6:$I$17,'S6'!$B$6:$B$17,$A47,'S6'!$E$6:$E$17,"Ambos")+SUMIFS('S7'!$I$6:$I$19,'S7'!$B$6:$B$19,$A47,'S7'!$E$6:$E$19,"Diego")+SUMIFS('S7'!$I$6:$I$19,'S7'!$B$6:$B$19,$A47,'S7'!$E$6:$E$19,"Ambos")+SUMIFS('S8'!$I$6:$I$23,'S8'!$B$6:$B$23,$A47,'S8'!$E$6:$E$23,"Diego")+SUMIFS('S8'!$I$6:$I$23,'S8'!$B$6:$B$23,$A47,'S8'!$E$6:$E$23,"Ambos")+SUMIFS('S9'!$I$6:$I$15,'S9'!$B$6:$B$15,$A47,'S9'!$E$6:$E$15,"Diego")+SUMIFS('S9'!$I$6:$I$15,'S9'!$B$6:$B$15,$A47,'S9'!$E$6:$E$15,"Ambos")+SUMIFS('S10'!$I$6:$I$13,'S10'!$B$6:$B$13,$A47,'S10'!$E$6:$E$13,"Diego")+SUMIFS('S10'!$I$6:$I$13,'S10'!$B$6:$B$13,$A47,'S10'!$E$6:$E$13,"Ambos")+SUMIFS('Holgura'!$I$6:$I$11,'Holgura'!$B$6:$B$11,$A47,'Holgura'!$E$6:$E$11,"Diego")+SUMIFS('Holgura'!$I$6:$I$11,'Holgura'!$B$6:$B$11,$A47,'Holgura'!$E$6:$E$11,"Ambos")+SUMIFS('Entrega'!$I$6:$I$9,'Entrega'!$B$6:$B$9,$A47,'Entrega'!$E$6:$E$9,"Diego")+SUMIFS('Entrega'!$I$6:$I$9,'Entrega'!$B$6:$B$9,$A47,'Entrega'!$E$6:$E$9,"Ambos")+SUMIFS('Defensa'!$I$6:$I$10,'Defensa'!$B$6:$B$10,$A47,'Defensa'!$E$6:$E$10,"Diego")+SUMIFS('Defensa'!$I$6:$I$10,'Defensa'!$B$6:$B$10,$A47,'Defensa'!$E$6:$E$10,"Ambos")</f>
         <v/>
       </c>
       <c r="F47" s="21">
-        <f>COUNTIFS('S1'!$B$6:$B$32,$A47,'S1'!$E$6:$E$32,"Víctor")+COUNTIFS('S1'!$B$6:$B$32,$A47,'S1'!$E$6:$E$32,"Ambos")+COUNTIFS('S2'!$B$6:$B$23,$A47,'S2'!$E$6:$E$23,"Víctor")+COUNTIFS('S2'!$B$6:$B$23,$A47,'S2'!$E$6:$E$23,"Ambos")+COUNTIFS('S3'!$B$6:$B$19,$A47,'S3'!$E$6:$E$19,"Víctor")+COUNTIFS('S3'!$B$6:$B$19,$A47,'S3'!$E$6:$E$19,"Ambos")+COUNTIFS('S4'!$B$6:$B$20,$A47,'S4'!$E$6:$E$20,"Víctor")+COUNTIFS('S4'!$B$6:$B$20,$A47,'S4'!$E$6:$E$20,"Ambos")+COUNTIFS('S5'!$B$6:$B$20,$A47,'S5'!$E$6:$E$20,"Víctor")+COUNTIFS('S5'!$B$6:$B$20,$A47,'S5'!$E$6:$E$20,"Ambos")+COUNTIFS('S6'!$B$6:$B$17,$A47,'S6'!$E$6:$E$17,"Víctor")+COUNTIFS('S6'!$B$6:$B$17,$A47,'S6'!$E$6:$E$17,"Ambos")+COUNTIFS('S7'!$B$6:$B$19,$A47,'S7'!$E$6:$E$19,"Víctor")+COUNTIFS('S7'!$B$6:$B$19,$A47,'S7'!$E$6:$E$19,"Ambos")+COUNTIFS('S8'!$B$6:$B$23,$A47,'S8'!$E$6:$E$23,"Víctor")+COUNTIFS('S8'!$B$6:$B$23,$A47,'S8'!$E$6:$E$23,"Ambos")+COUNTIFS('S9'!$B$6:$B$15,$A47,'S9'!$E$6:$E$15,"Víctor")+COUNTIFS('S9'!$B$6:$B$15,$A47,'S9'!$E$6:$E$15,"Ambos")+COUNTIFS('S10'!$B$6:$B$13,$A47,'S10'!$E$6:$E$13,"Víctor")+COUNTIFS('S10'!$B$6:$B$13,$A47,'S10'!$E$6:$E$13,"Ambos")+COUNTIFS('Holgura'!$B$6:$B$11,$A47,'Holgura'!$E$6:$E$11,"Víctor")+COUNTIFS('Holgura'!$B$6:$B$11,$A47,'Holgura'!$E$6:$E$11,"Ambos")+COUNTIFS('Entrega'!$B$6:$B$9,$A47,'Entrega'!$E$6:$E$9,"Víctor")+COUNTIFS('Entrega'!$B$6:$B$9,$A47,'Entrega'!$E$6:$E$9,"Ambos")+COUNTIFS('Defensa'!$B$6:$B$10,$A47,'Defensa'!$E$6:$E$10,"Víctor")+COUNTIFS('Defensa'!$B$6:$B$10,$A47,'Defensa'!$E$6:$E$10,"Ambos")</f>
+        <f>COUNTIFS('S1'!$B$6:$B$32,$A47,'S1'!$E$6:$E$32,"Víctor")+COUNTIFS('S1'!$B$6:$B$32,$A47,'S1'!$E$6:$E$32,"Ambos")+COUNTIFS('S2'!$B$6:$B$23,$A47,'S2'!$E$6:$E$23,"Víctor")+COUNTIFS('S2'!$B$6:$B$23,$A47,'S2'!$E$6:$E$23,"Ambos")+COUNTIFS('S3'!$B$6:$B$24,$A47,'S3'!$E$6:$E$24,"Víctor")+COUNTIFS('S3'!$B$6:$B$24,$A47,'S3'!$E$6:$E$24,"Ambos")+COUNTIFS('S4'!$B$6:$B$22,$A47,'S4'!$E$6:$E$22,"Víctor")+COUNTIFS('S4'!$B$6:$B$22,$A47,'S4'!$E$6:$E$22,"Ambos")+COUNTIFS('S5'!$B$6:$B$20,$A47,'S5'!$E$6:$E$20,"Víctor")+COUNTIFS('S5'!$B$6:$B$20,$A47,'S5'!$E$6:$E$20,"Ambos")+COUNTIFS('S6'!$B$6:$B$17,$A47,'S6'!$E$6:$E$17,"Víctor")+COUNTIFS('S6'!$B$6:$B$17,$A47,'S6'!$E$6:$E$17,"Ambos")+COUNTIFS('S7'!$B$6:$B$19,$A47,'S7'!$E$6:$E$19,"Víctor")+COUNTIFS('S7'!$B$6:$B$19,$A47,'S7'!$E$6:$E$19,"Ambos")+COUNTIFS('S8'!$B$6:$B$23,$A47,'S8'!$E$6:$E$23,"Víctor")+COUNTIFS('S8'!$B$6:$B$23,$A47,'S8'!$E$6:$E$23,"Ambos")+COUNTIFS('S9'!$B$6:$B$15,$A47,'S9'!$E$6:$E$15,"Víctor")+COUNTIFS('S9'!$B$6:$B$15,$A47,'S9'!$E$6:$E$15,"Ambos")+COUNTIFS('S10'!$B$6:$B$13,$A47,'S10'!$E$6:$E$13,"Víctor")+COUNTIFS('S10'!$B$6:$B$13,$A47,'S10'!$E$6:$E$13,"Ambos")+COUNTIFS('Holgura'!$B$6:$B$11,$A47,'Holgura'!$E$6:$E$11,"Víctor")+COUNTIFS('Holgura'!$B$6:$B$11,$A47,'Holgura'!$E$6:$E$11,"Ambos")+COUNTIFS('Entrega'!$B$6:$B$9,$A47,'Entrega'!$E$6:$E$9,"Víctor")+COUNTIFS('Entrega'!$B$6:$B$9,$A47,'Entrega'!$E$6:$E$9,"Ambos")+COUNTIFS('Defensa'!$B$6:$B$10,$A47,'Defensa'!$E$6:$E$10,"Víctor")+COUNTIFS('Defensa'!$B$6:$B$10,$A47,'Defensa'!$E$6:$E$10,"Ambos")</f>
         <v/>
       </c>
       <c r="G47" s="21">
-        <f>COUNTIFS('S1'!$B$6:$B$32,$A47,'S1'!$E$6:$E$32,"Diego")+COUNTIFS('S1'!$B$6:$B$32,$A47,'S1'!$E$6:$E$32,"Ambos")+COUNTIFS('S2'!$B$6:$B$23,$A47,'S2'!$E$6:$E$23,"Diego")+COUNTIFS('S2'!$B$6:$B$23,$A47,'S2'!$E$6:$E$23,"Ambos")+COUNTIFS('S3'!$B$6:$B$19,$A47,'S3'!$E$6:$E$19,"Diego")+COUNTIFS('S3'!$B$6:$B$19,$A47,'S3'!$E$6:$E$19,"Ambos")+COUNTIFS('S4'!$B$6:$B$20,$A47,'S4'!$E$6:$E$20,"Diego")+COUNTIFS('S4'!$B$6:$B$20,$A47,'S4'!$E$6:$E$20,"Ambos")+COUNTIFS('S5'!$B$6:$B$20,$A47,'S5'!$E$6:$E$20,"Diego")+COUNTIFS('S5'!$B$6:$B$20,$A47,'S5'!$E$6:$E$20,"Ambos")+COUNTIFS('S6'!$B$6:$B$17,$A47,'S6'!$E$6:$E$17,"Diego")+COUNTIFS('S6'!$B$6:$B$17,$A47,'S6'!$E$6:$E$17,"Ambos")+COUNTIFS('S7'!$B$6:$B$19,$A47,'S7'!$E$6:$E$19,"Diego")+COUNTIFS('S7'!$B$6:$B$19,$A47,'S7'!$E$6:$E$19,"Ambos")+COUNTIFS('S8'!$B$6:$B$23,$A47,'S8'!$E$6:$E$23,"Diego")+COUNTIFS('S8'!$B$6:$B$23,$A47,'S8'!$E$6:$E$23,"Ambos")+COUNTIFS('S9'!$B$6:$B$15,$A47,'S9'!$E$6:$E$15,"Diego")+COUNTIFS('S9'!$B$6:$B$15,$A47,'S9'!$E$6:$E$15,"Ambos")+COUNTIFS('S10'!$B$6:$B$13,$A47,'S10'!$E$6:$E$13,"Diego")+COUNTIFS('S10'!$B$6:$B$13,$A47,'S10'!$E$6:$E$13,"Ambos")+COUNTIFS('Holgura'!$B$6:$B$11,$A47,'Holgura'!$E$6:$E$11,"Diego")+COUNTIFS('Holgura'!$B$6:$B$11,$A47,'Holgura'!$E$6:$E$11,"Ambos")+COUNTIFS('Entrega'!$B$6:$B$9,$A47,'Entrega'!$E$6:$E$9,"Diego")+COUNTIFS('Entrega'!$B$6:$B$9,$A47,'Entrega'!$E$6:$E$9,"Ambos")+COUNTIFS('Defensa'!$B$6:$B$10,$A47,'Defensa'!$E$6:$E$10,"Diego")+COUNTIFS('Defensa'!$B$6:$B$10,$A47,'Defensa'!$E$6:$E$10,"Ambos")</f>
+        <f>COUNTIFS('S1'!$B$6:$B$32,$A47,'S1'!$E$6:$E$32,"Diego")+COUNTIFS('S1'!$B$6:$B$32,$A47,'S1'!$E$6:$E$32,"Ambos")+COUNTIFS('S2'!$B$6:$B$23,$A47,'S2'!$E$6:$E$23,"Diego")+COUNTIFS('S2'!$B$6:$B$23,$A47,'S2'!$E$6:$E$23,"Ambos")+COUNTIFS('S3'!$B$6:$B$24,$A47,'S3'!$E$6:$E$24,"Diego")+COUNTIFS('S3'!$B$6:$B$24,$A47,'S3'!$E$6:$E$24,"Ambos")+COUNTIFS('S4'!$B$6:$B$22,$A47,'S4'!$E$6:$E$22,"Diego")+COUNTIFS('S4'!$B$6:$B$22,$A47,'S4'!$E$6:$E$22,"Ambos")+COUNTIFS('S5'!$B$6:$B$20,$A47,'S5'!$E$6:$E$20,"Diego")+COUNTIFS('S5'!$B$6:$B$20,$A47,'S5'!$E$6:$E$20,"Ambos")+COUNTIFS('S6'!$B$6:$B$17,$A47,'S6'!$E$6:$E$17,"Diego")+COUNTIFS('S6'!$B$6:$B$17,$A47,'S6'!$E$6:$E$17,"Ambos")+COUNTIFS('S7'!$B$6:$B$19,$A47,'S7'!$E$6:$E$19,"Diego")+COUNTIFS('S7'!$B$6:$B$19,$A47,'S7'!$E$6:$E$19,"Ambos")+COUNTIFS('S8'!$B$6:$B$23,$A47,'S8'!$E$6:$E$23,"Diego")+COUNTIFS('S8'!$B$6:$B$23,$A47,'S8'!$E$6:$E$23,"Ambos")+COUNTIFS('S9'!$B$6:$B$15,$A47,'S9'!$E$6:$E$15,"Diego")+COUNTIFS('S9'!$B$6:$B$15,$A47,'S9'!$E$6:$E$15,"Ambos")+COUNTIFS('S10'!$B$6:$B$13,$A47,'S10'!$E$6:$E$13,"Diego")+COUNTIFS('S10'!$B$6:$B$13,$A47,'S10'!$E$6:$E$13,"Ambos")+COUNTIFS('Holgura'!$B$6:$B$11,$A47,'Holgura'!$E$6:$E$11,"Diego")+COUNTIFS('Holgura'!$B$6:$B$11,$A47,'Holgura'!$E$6:$E$11,"Ambos")+COUNTIFS('Entrega'!$B$6:$B$9,$A47,'Entrega'!$E$6:$E$9,"Diego")+COUNTIFS('Entrega'!$B$6:$B$9,$A47,'Entrega'!$E$6:$E$9,"Ambos")+COUNTIFS('Defensa'!$B$6:$B$10,$A47,'Defensa'!$E$6:$E$10,"Diego")+COUNTIFS('Defensa'!$B$6:$B$10,$A47,'Defensa'!$E$6:$E$10,"Ambos")</f>
         <v/>
       </c>
     </row>
@@ -9927,19 +9948,19 @@
         <v/>
       </c>
       <c r="D48" s="21">
-        <f>SUMIFS('S1'!$I$6:$I$32,'S1'!$B$6:$B$32,$A48,'S1'!$E$6:$E$32,"Víctor")+SUMIFS('S1'!$I$6:$I$32,'S1'!$B$6:$B$32,$A48,'S1'!$E$6:$E$32,"Ambos")+SUMIFS('S2'!$I$6:$I$23,'S2'!$B$6:$B$23,$A48,'S2'!$E$6:$E$23,"Víctor")+SUMIFS('S2'!$I$6:$I$23,'S2'!$B$6:$B$23,$A48,'S2'!$E$6:$E$23,"Ambos")+SUMIFS('S3'!$I$6:$I$19,'S3'!$B$6:$B$19,$A48,'S3'!$E$6:$E$19,"Víctor")+SUMIFS('S3'!$I$6:$I$19,'S3'!$B$6:$B$19,$A48,'S3'!$E$6:$E$19,"Ambos")+SUMIFS('S4'!$I$6:$I$20,'S4'!$B$6:$B$20,$A48,'S4'!$E$6:$E$20,"Víctor")+SUMIFS('S4'!$I$6:$I$20,'S4'!$B$6:$B$20,$A48,'S4'!$E$6:$E$20,"Ambos")+SUMIFS('S5'!$I$6:$I$20,'S5'!$B$6:$B$20,$A48,'S5'!$E$6:$E$20,"Víctor")+SUMIFS('S5'!$I$6:$I$20,'S5'!$B$6:$B$20,$A48,'S5'!$E$6:$E$20,"Ambos")+SUMIFS('S6'!$I$6:$I$17,'S6'!$B$6:$B$17,$A48,'S6'!$E$6:$E$17,"Víctor")+SUMIFS('S6'!$I$6:$I$17,'S6'!$B$6:$B$17,$A48,'S6'!$E$6:$E$17,"Ambos")+SUMIFS('S7'!$I$6:$I$19,'S7'!$B$6:$B$19,$A48,'S7'!$E$6:$E$19,"Víctor")+SUMIFS('S7'!$I$6:$I$19,'S7'!$B$6:$B$19,$A48,'S7'!$E$6:$E$19,"Ambos")+SUMIFS('S8'!$I$6:$I$23,'S8'!$B$6:$B$23,$A48,'S8'!$E$6:$E$23,"Víctor")+SUMIFS('S8'!$I$6:$I$23,'S8'!$B$6:$B$23,$A48,'S8'!$E$6:$E$23,"Ambos")+SUMIFS('S9'!$I$6:$I$15,'S9'!$B$6:$B$15,$A48,'S9'!$E$6:$E$15,"Víctor")+SUMIFS('S9'!$I$6:$I$15,'S9'!$B$6:$B$15,$A48,'S9'!$E$6:$E$15,"Ambos")+SUMIFS('S10'!$I$6:$I$13,'S10'!$B$6:$B$13,$A48,'S10'!$E$6:$E$13,"Víctor")+SUMIFS('S10'!$I$6:$I$13,'S10'!$B$6:$B$13,$A48,'S10'!$E$6:$E$13,"Ambos")+SUMIFS('Holgura'!$I$6:$I$11,'Holgura'!$B$6:$B$11,$A48,'Holgura'!$E$6:$E$11,"Víctor")+SUMIFS('Holgura'!$I$6:$I$11,'Holgura'!$B$6:$B$11,$A48,'Holgura'!$E$6:$E$11,"Ambos")+SUMIFS('Entrega'!$I$6:$I$9,'Entrega'!$B$6:$B$9,$A48,'Entrega'!$E$6:$E$9,"Víctor")+SUMIFS('Entrega'!$I$6:$I$9,'Entrega'!$B$6:$B$9,$A48,'Entrega'!$E$6:$E$9,"Ambos")+SUMIFS('Defensa'!$I$6:$I$10,'Defensa'!$B$6:$B$10,$A48,'Defensa'!$E$6:$E$10,"Víctor")+SUMIFS('Defensa'!$I$6:$I$10,'Defensa'!$B$6:$B$10,$A48,'Defensa'!$E$6:$E$10,"Ambos")</f>
+        <f>SUMIFS('S1'!$I$6:$I$32,'S1'!$B$6:$B$32,$A48,'S1'!$E$6:$E$32,"Víctor")+SUMIFS('S1'!$I$6:$I$32,'S1'!$B$6:$B$32,$A48,'S1'!$E$6:$E$32,"Ambos")+SUMIFS('S2'!$I$6:$I$23,'S2'!$B$6:$B$23,$A48,'S2'!$E$6:$E$23,"Víctor")+SUMIFS('S2'!$I$6:$I$23,'S2'!$B$6:$B$23,$A48,'S2'!$E$6:$E$23,"Ambos")+SUMIFS('S3'!$I$6:$I$24,'S3'!$B$6:$B$24,$A48,'S3'!$E$6:$E$24,"Víctor")+SUMIFS('S3'!$I$6:$I$24,'S3'!$B$6:$B$24,$A48,'S3'!$E$6:$E$24,"Ambos")+SUMIFS('S4'!$I$6:$I$22,'S4'!$B$6:$B$22,$A48,'S4'!$E$6:$E$22,"Víctor")+SUMIFS('S4'!$I$6:$I$22,'S4'!$B$6:$B$22,$A48,'S4'!$E$6:$E$22,"Ambos")+SUMIFS('S5'!$I$6:$I$20,'S5'!$B$6:$B$20,$A48,'S5'!$E$6:$E$20,"Víctor")+SUMIFS('S5'!$I$6:$I$20,'S5'!$B$6:$B$20,$A48,'S5'!$E$6:$E$20,"Ambos")+SUMIFS('S6'!$I$6:$I$17,'S6'!$B$6:$B$17,$A48,'S6'!$E$6:$E$17,"Víctor")+SUMIFS('S6'!$I$6:$I$17,'S6'!$B$6:$B$17,$A48,'S6'!$E$6:$E$17,"Ambos")+SUMIFS('S7'!$I$6:$I$19,'S7'!$B$6:$B$19,$A48,'S7'!$E$6:$E$19,"Víctor")+SUMIFS('S7'!$I$6:$I$19,'S7'!$B$6:$B$19,$A48,'S7'!$E$6:$E$19,"Ambos")+SUMIFS('S8'!$I$6:$I$23,'S8'!$B$6:$B$23,$A48,'S8'!$E$6:$E$23,"Víctor")+SUMIFS('S8'!$I$6:$I$23,'S8'!$B$6:$B$23,$A48,'S8'!$E$6:$E$23,"Ambos")+SUMIFS('S9'!$I$6:$I$15,'S9'!$B$6:$B$15,$A48,'S9'!$E$6:$E$15,"Víctor")+SUMIFS('S9'!$I$6:$I$15,'S9'!$B$6:$B$15,$A48,'S9'!$E$6:$E$15,"Ambos")+SUMIFS('S10'!$I$6:$I$13,'S10'!$B$6:$B$13,$A48,'S10'!$E$6:$E$13,"Víctor")+SUMIFS('S10'!$I$6:$I$13,'S10'!$B$6:$B$13,$A48,'S10'!$E$6:$E$13,"Ambos")+SUMIFS('Holgura'!$I$6:$I$11,'Holgura'!$B$6:$B$11,$A48,'Holgura'!$E$6:$E$11,"Víctor")+SUMIFS('Holgura'!$I$6:$I$11,'Holgura'!$B$6:$B$11,$A48,'Holgura'!$E$6:$E$11,"Ambos")+SUMIFS('Entrega'!$I$6:$I$9,'Entrega'!$B$6:$B$9,$A48,'Entrega'!$E$6:$E$9,"Víctor")+SUMIFS('Entrega'!$I$6:$I$9,'Entrega'!$B$6:$B$9,$A48,'Entrega'!$E$6:$E$9,"Ambos")+SUMIFS('Defensa'!$I$6:$I$10,'Defensa'!$B$6:$B$10,$A48,'Defensa'!$E$6:$E$10,"Víctor")+SUMIFS('Defensa'!$I$6:$I$10,'Defensa'!$B$6:$B$10,$A48,'Defensa'!$E$6:$E$10,"Ambos")</f>
         <v/>
       </c>
       <c r="E48" s="21">
-        <f>SUMIFS('S1'!$I$6:$I$32,'S1'!$B$6:$B$32,$A48,'S1'!$E$6:$E$32,"Diego")+SUMIFS('S1'!$I$6:$I$32,'S1'!$B$6:$B$32,$A48,'S1'!$E$6:$E$32,"Ambos")+SUMIFS('S2'!$I$6:$I$23,'S2'!$B$6:$B$23,$A48,'S2'!$E$6:$E$23,"Diego")+SUMIFS('S2'!$I$6:$I$23,'S2'!$B$6:$B$23,$A48,'S2'!$E$6:$E$23,"Ambos")+SUMIFS('S3'!$I$6:$I$19,'S3'!$B$6:$B$19,$A48,'S3'!$E$6:$E$19,"Diego")+SUMIFS('S3'!$I$6:$I$19,'S3'!$B$6:$B$19,$A48,'S3'!$E$6:$E$19,"Ambos")+SUMIFS('S4'!$I$6:$I$20,'S4'!$B$6:$B$20,$A48,'S4'!$E$6:$E$20,"Diego")+SUMIFS('S4'!$I$6:$I$20,'S4'!$B$6:$B$20,$A48,'S4'!$E$6:$E$20,"Ambos")+SUMIFS('S5'!$I$6:$I$20,'S5'!$B$6:$B$20,$A48,'S5'!$E$6:$E$20,"Diego")+SUMIFS('S5'!$I$6:$I$20,'S5'!$B$6:$B$20,$A48,'S5'!$E$6:$E$20,"Ambos")+SUMIFS('S6'!$I$6:$I$17,'S6'!$B$6:$B$17,$A48,'S6'!$E$6:$E$17,"Diego")+SUMIFS('S6'!$I$6:$I$17,'S6'!$B$6:$B$17,$A48,'S6'!$E$6:$E$17,"Ambos")+SUMIFS('S7'!$I$6:$I$19,'S7'!$B$6:$B$19,$A48,'S7'!$E$6:$E$19,"Diego")+SUMIFS('S7'!$I$6:$I$19,'S7'!$B$6:$B$19,$A48,'S7'!$E$6:$E$19,"Ambos")+SUMIFS('S8'!$I$6:$I$23,'S8'!$B$6:$B$23,$A48,'S8'!$E$6:$E$23,"Diego")+SUMIFS('S8'!$I$6:$I$23,'S8'!$B$6:$B$23,$A48,'S8'!$E$6:$E$23,"Ambos")+SUMIFS('S9'!$I$6:$I$15,'S9'!$B$6:$B$15,$A48,'S9'!$E$6:$E$15,"Diego")+SUMIFS('S9'!$I$6:$I$15,'S9'!$B$6:$B$15,$A48,'S9'!$E$6:$E$15,"Ambos")+SUMIFS('S10'!$I$6:$I$13,'S10'!$B$6:$B$13,$A48,'S10'!$E$6:$E$13,"Diego")+SUMIFS('S10'!$I$6:$I$13,'S10'!$B$6:$B$13,$A48,'S10'!$E$6:$E$13,"Ambos")+SUMIFS('Holgura'!$I$6:$I$11,'Holgura'!$B$6:$B$11,$A48,'Holgura'!$E$6:$E$11,"Diego")+SUMIFS('Holgura'!$I$6:$I$11,'Holgura'!$B$6:$B$11,$A48,'Holgura'!$E$6:$E$11,"Ambos")+SUMIFS('Entrega'!$I$6:$I$9,'Entrega'!$B$6:$B$9,$A48,'Entrega'!$E$6:$E$9,"Diego")+SUMIFS('Entrega'!$I$6:$I$9,'Entrega'!$B$6:$B$9,$A48,'Entrega'!$E$6:$E$9,"Ambos")+SUMIFS('Defensa'!$I$6:$I$10,'Defensa'!$B$6:$B$10,$A48,'Defensa'!$E$6:$E$10,"Diego")+SUMIFS('Defensa'!$I$6:$I$10,'Defensa'!$B$6:$B$10,$A48,'Defensa'!$E$6:$E$10,"Ambos")</f>
+        <f>SUMIFS('S1'!$I$6:$I$32,'S1'!$B$6:$B$32,$A48,'S1'!$E$6:$E$32,"Diego")+SUMIFS('S1'!$I$6:$I$32,'S1'!$B$6:$B$32,$A48,'S1'!$E$6:$E$32,"Ambos")+SUMIFS('S2'!$I$6:$I$23,'S2'!$B$6:$B$23,$A48,'S2'!$E$6:$E$23,"Diego")+SUMIFS('S2'!$I$6:$I$23,'S2'!$B$6:$B$23,$A48,'S2'!$E$6:$E$23,"Ambos")+SUMIFS('S3'!$I$6:$I$24,'S3'!$B$6:$B$24,$A48,'S3'!$E$6:$E$24,"Diego")+SUMIFS('S3'!$I$6:$I$24,'S3'!$B$6:$B$24,$A48,'S3'!$E$6:$E$24,"Ambos")+SUMIFS('S4'!$I$6:$I$22,'S4'!$B$6:$B$22,$A48,'S4'!$E$6:$E$22,"Diego")+SUMIFS('S4'!$I$6:$I$22,'S4'!$B$6:$B$22,$A48,'S4'!$E$6:$E$22,"Ambos")+SUMIFS('S5'!$I$6:$I$20,'S5'!$B$6:$B$20,$A48,'S5'!$E$6:$E$20,"Diego")+SUMIFS('S5'!$I$6:$I$20,'S5'!$B$6:$B$20,$A48,'S5'!$E$6:$E$20,"Ambos")+SUMIFS('S6'!$I$6:$I$17,'S6'!$B$6:$B$17,$A48,'S6'!$E$6:$E$17,"Diego")+SUMIFS('S6'!$I$6:$I$17,'S6'!$B$6:$B$17,$A48,'S6'!$E$6:$E$17,"Ambos")+SUMIFS('S7'!$I$6:$I$19,'S7'!$B$6:$B$19,$A48,'S7'!$E$6:$E$19,"Diego")+SUMIFS('S7'!$I$6:$I$19,'S7'!$B$6:$B$19,$A48,'S7'!$E$6:$E$19,"Ambos")+SUMIFS('S8'!$I$6:$I$23,'S8'!$B$6:$B$23,$A48,'S8'!$E$6:$E$23,"Diego")+SUMIFS('S8'!$I$6:$I$23,'S8'!$B$6:$B$23,$A48,'S8'!$E$6:$E$23,"Ambos")+SUMIFS('S9'!$I$6:$I$15,'S9'!$B$6:$B$15,$A48,'S9'!$E$6:$E$15,"Diego")+SUMIFS('S9'!$I$6:$I$15,'S9'!$B$6:$B$15,$A48,'S9'!$E$6:$E$15,"Ambos")+SUMIFS('S10'!$I$6:$I$13,'S10'!$B$6:$B$13,$A48,'S10'!$E$6:$E$13,"Diego")+SUMIFS('S10'!$I$6:$I$13,'S10'!$B$6:$B$13,$A48,'S10'!$E$6:$E$13,"Ambos")+SUMIFS('Holgura'!$I$6:$I$11,'Holgura'!$B$6:$B$11,$A48,'Holgura'!$E$6:$E$11,"Diego")+SUMIFS('Holgura'!$I$6:$I$11,'Holgura'!$B$6:$B$11,$A48,'Holgura'!$E$6:$E$11,"Ambos")+SUMIFS('Entrega'!$I$6:$I$9,'Entrega'!$B$6:$B$9,$A48,'Entrega'!$E$6:$E$9,"Diego")+SUMIFS('Entrega'!$I$6:$I$9,'Entrega'!$B$6:$B$9,$A48,'Entrega'!$E$6:$E$9,"Ambos")+SUMIFS('Defensa'!$I$6:$I$10,'Defensa'!$B$6:$B$10,$A48,'Defensa'!$E$6:$E$10,"Diego")+SUMIFS('Defensa'!$I$6:$I$10,'Defensa'!$B$6:$B$10,$A48,'Defensa'!$E$6:$E$10,"Ambos")</f>
         <v/>
       </c>
       <c r="F48" s="21">
-        <f>COUNTIFS('S1'!$B$6:$B$32,$A48,'S1'!$E$6:$E$32,"Víctor")+COUNTIFS('S1'!$B$6:$B$32,$A48,'S1'!$E$6:$E$32,"Ambos")+COUNTIFS('S2'!$B$6:$B$23,$A48,'S2'!$E$6:$E$23,"Víctor")+COUNTIFS('S2'!$B$6:$B$23,$A48,'S2'!$E$6:$E$23,"Ambos")+COUNTIFS('S3'!$B$6:$B$19,$A48,'S3'!$E$6:$E$19,"Víctor")+COUNTIFS('S3'!$B$6:$B$19,$A48,'S3'!$E$6:$E$19,"Ambos")+COUNTIFS('S4'!$B$6:$B$20,$A48,'S4'!$E$6:$E$20,"Víctor")+COUNTIFS('S4'!$B$6:$B$20,$A48,'S4'!$E$6:$E$20,"Ambos")+COUNTIFS('S5'!$B$6:$B$20,$A48,'S5'!$E$6:$E$20,"Víctor")+COUNTIFS('S5'!$B$6:$B$20,$A48,'S5'!$E$6:$E$20,"Ambos")+COUNTIFS('S6'!$B$6:$B$17,$A48,'S6'!$E$6:$E$17,"Víctor")+COUNTIFS('S6'!$B$6:$B$17,$A48,'S6'!$E$6:$E$17,"Ambos")+COUNTIFS('S7'!$B$6:$B$19,$A48,'S7'!$E$6:$E$19,"Víctor")+COUNTIFS('S7'!$B$6:$B$19,$A48,'S7'!$E$6:$E$19,"Ambos")+COUNTIFS('S8'!$B$6:$B$23,$A48,'S8'!$E$6:$E$23,"Víctor")+COUNTIFS('S8'!$B$6:$B$23,$A48,'S8'!$E$6:$E$23,"Ambos")+COUNTIFS('S9'!$B$6:$B$15,$A48,'S9'!$E$6:$E$15,"Víctor")+COUNTIFS('S9'!$B$6:$B$15,$A48,'S9'!$E$6:$E$15,"Ambos")+COUNTIFS('S10'!$B$6:$B$13,$A48,'S10'!$E$6:$E$13,"Víctor")+COUNTIFS('S10'!$B$6:$B$13,$A48,'S10'!$E$6:$E$13,"Ambos")+COUNTIFS('Holgura'!$B$6:$B$11,$A48,'Holgura'!$E$6:$E$11,"Víctor")+COUNTIFS('Holgura'!$B$6:$B$11,$A48,'Holgura'!$E$6:$E$11,"Ambos")+COUNTIFS('Entrega'!$B$6:$B$9,$A48,'Entrega'!$E$6:$E$9,"Víctor")+COUNTIFS('Entrega'!$B$6:$B$9,$A48,'Entrega'!$E$6:$E$9,"Ambos")+COUNTIFS('Defensa'!$B$6:$B$10,$A48,'Defensa'!$E$6:$E$10,"Víctor")+COUNTIFS('Defensa'!$B$6:$B$10,$A48,'Defensa'!$E$6:$E$10,"Ambos")</f>
+        <f>COUNTIFS('S1'!$B$6:$B$32,$A48,'S1'!$E$6:$E$32,"Víctor")+COUNTIFS('S1'!$B$6:$B$32,$A48,'S1'!$E$6:$E$32,"Ambos")+COUNTIFS('S2'!$B$6:$B$23,$A48,'S2'!$E$6:$E$23,"Víctor")+COUNTIFS('S2'!$B$6:$B$23,$A48,'S2'!$E$6:$E$23,"Ambos")+COUNTIFS('S3'!$B$6:$B$24,$A48,'S3'!$E$6:$E$24,"Víctor")+COUNTIFS('S3'!$B$6:$B$24,$A48,'S3'!$E$6:$E$24,"Ambos")+COUNTIFS('S4'!$B$6:$B$22,$A48,'S4'!$E$6:$E$22,"Víctor")+COUNTIFS('S4'!$B$6:$B$22,$A48,'S4'!$E$6:$E$22,"Ambos")+COUNTIFS('S5'!$B$6:$B$20,$A48,'S5'!$E$6:$E$20,"Víctor")+COUNTIFS('S5'!$B$6:$B$20,$A48,'S5'!$E$6:$E$20,"Ambos")+COUNTIFS('S6'!$B$6:$B$17,$A48,'S6'!$E$6:$E$17,"Víctor")+COUNTIFS('S6'!$B$6:$B$17,$A48,'S6'!$E$6:$E$17,"Ambos")+COUNTIFS('S7'!$B$6:$B$19,$A48,'S7'!$E$6:$E$19,"Víctor")+COUNTIFS('S7'!$B$6:$B$19,$A48,'S7'!$E$6:$E$19,"Ambos")+COUNTIFS('S8'!$B$6:$B$23,$A48,'S8'!$E$6:$E$23,"Víctor")+COUNTIFS('S8'!$B$6:$B$23,$A48,'S8'!$E$6:$E$23,"Ambos")+COUNTIFS('S9'!$B$6:$B$15,$A48,'S9'!$E$6:$E$15,"Víctor")+COUNTIFS('S9'!$B$6:$B$15,$A48,'S9'!$E$6:$E$15,"Ambos")+COUNTIFS('S10'!$B$6:$B$13,$A48,'S10'!$E$6:$E$13,"Víctor")+COUNTIFS('S10'!$B$6:$B$13,$A48,'S10'!$E$6:$E$13,"Ambos")+COUNTIFS('Holgura'!$B$6:$B$11,$A48,'Holgura'!$E$6:$E$11,"Víctor")+COUNTIFS('Holgura'!$B$6:$B$11,$A48,'Holgura'!$E$6:$E$11,"Ambos")+COUNTIFS('Entrega'!$B$6:$B$9,$A48,'Entrega'!$E$6:$E$9,"Víctor")+COUNTIFS('Entrega'!$B$6:$B$9,$A48,'Entrega'!$E$6:$E$9,"Ambos")+COUNTIFS('Defensa'!$B$6:$B$10,$A48,'Defensa'!$E$6:$E$10,"Víctor")+COUNTIFS('Defensa'!$B$6:$B$10,$A48,'Defensa'!$E$6:$E$10,"Ambos")</f>
         <v/>
       </c>
       <c r="G48" s="21">
-        <f>COUNTIFS('S1'!$B$6:$B$32,$A48,'S1'!$E$6:$E$32,"Diego")+COUNTIFS('S1'!$B$6:$B$32,$A48,'S1'!$E$6:$E$32,"Ambos")+COUNTIFS('S2'!$B$6:$B$23,$A48,'S2'!$E$6:$E$23,"Diego")+COUNTIFS('S2'!$B$6:$B$23,$A48,'S2'!$E$6:$E$23,"Ambos")+COUNTIFS('S3'!$B$6:$B$19,$A48,'S3'!$E$6:$E$19,"Diego")+COUNTIFS('S3'!$B$6:$B$19,$A48,'S3'!$E$6:$E$19,"Ambos")+COUNTIFS('S4'!$B$6:$B$20,$A48,'S4'!$E$6:$E$20,"Diego")+COUNTIFS('S4'!$B$6:$B$20,$A48,'S4'!$E$6:$E$20,"Ambos")+COUNTIFS('S5'!$B$6:$B$20,$A48,'S5'!$E$6:$E$20,"Diego")+COUNTIFS('S5'!$B$6:$B$20,$A48,'S5'!$E$6:$E$20,"Ambos")+COUNTIFS('S6'!$B$6:$B$17,$A48,'S6'!$E$6:$E$17,"Diego")+COUNTIFS('S6'!$B$6:$B$17,$A48,'S6'!$E$6:$E$17,"Ambos")+COUNTIFS('S7'!$B$6:$B$19,$A48,'S7'!$E$6:$E$19,"Diego")+COUNTIFS('S7'!$B$6:$B$19,$A48,'S7'!$E$6:$E$19,"Ambos")+COUNTIFS('S8'!$B$6:$B$23,$A48,'S8'!$E$6:$E$23,"Diego")+COUNTIFS('S8'!$B$6:$B$23,$A48,'S8'!$E$6:$E$23,"Ambos")+COUNTIFS('S9'!$B$6:$B$15,$A48,'S9'!$E$6:$E$15,"Diego")+COUNTIFS('S9'!$B$6:$B$15,$A48,'S9'!$E$6:$E$15,"Ambos")+COUNTIFS('S10'!$B$6:$B$13,$A48,'S10'!$E$6:$E$13,"Diego")+COUNTIFS('S10'!$B$6:$B$13,$A48,'S10'!$E$6:$E$13,"Ambos")+COUNTIFS('Holgura'!$B$6:$B$11,$A48,'Holgura'!$E$6:$E$11,"Diego")+COUNTIFS('Holgura'!$B$6:$B$11,$A48,'Holgura'!$E$6:$E$11,"Ambos")+COUNTIFS('Entrega'!$B$6:$B$9,$A48,'Entrega'!$E$6:$E$9,"Diego")+COUNTIFS('Entrega'!$B$6:$B$9,$A48,'Entrega'!$E$6:$E$9,"Ambos")+COUNTIFS('Defensa'!$B$6:$B$10,$A48,'Defensa'!$E$6:$E$10,"Diego")+COUNTIFS('Defensa'!$B$6:$B$10,$A48,'Defensa'!$E$6:$E$10,"Ambos")</f>
+        <f>COUNTIFS('S1'!$B$6:$B$32,$A48,'S1'!$E$6:$E$32,"Diego")+COUNTIFS('S1'!$B$6:$B$32,$A48,'S1'!$E$6:$E$32,"Ambos")+COUNTIFS('S2'!$B$6:$B$23,$A48,'S2'!$E$6:$E$23,"Diego")+COUNTIFS('S2'!$B$6:$B$23,$A48,'S2'!$E$6:$E$23,"Ambos")+COUNTIFS('S3'!$B$6:$B$24,$A48,'S3'!$E$6:$E$24,"Diego")+COUNTIFS('S3'!$B$6:$B$24,$A48,'S3'!$E$6:$E$24,"Ambos")+COUNTIFS('S4'!$B$6:$B$22,$A48,'S4'!$E$6:$E$22,"Diego")+COUNTIFS('S4'!$B$6:$B$22,$A48,'S4'!$E$6:$E$22,"Ambos")+COUNTIFS('S5'!$B$6:$B$20,$A48,'S5'!$E$6:$E$20,"Diego")+COUNTIFS('S5'!$B$6:$B$20,$A48,'S5'!$E$6:$E$20,"Ambos")+COUNTIFS('S6'!$B$6:$B$17,$A48,'S6'!$E$6:$E$17,"Diego")+COUNTIFS('S6'!$B$6:$B$17,$A48,'S6'!$E$6:$E$17,"Ambos")+COUNTIFS('S7'!$B$6:$B$19,$A48,'S7'!$E$6:$E$19,"Diego")+COUNTIFS('S7'!$B$6:$B$19,$A48,'S7'!$E$6:$E$19,"Ambos")+COUNTIFS('S8'!$B$6:$B$23,$A48,'S8'!$E$6:$E$23,"Diego")+COUNTIFS('S8'!$B$6:$B$23,$A48,'S8'!$E$6:$E$23,"Ambos")+COUNTIFS('S9'!$B$6:$B$15,$A48,'S9'!$E$6:$E$15,"Diego")+COUNTIFS('S9'!$B$6:$B$15,$A48,'S9'!$E$6:$E$15,"Ambos")+COUNTIFS('S10'!$B$6:$B$13,$A48,'S10'!$E$6:$E$13,"Diego")+COUNTIFS('S10'!$B$6:$B$13,$A48,'S10'!$E$6:$E$13,"Ambos")+COUNTIFS('Holgura'!$B$6:$B$11,$A48,'Holgura'!$E$6:$E$11,"Diego")+COUNTIFS('Holgura'!$B$6:$B$11,$A48,'Holgura'!$E$6:$E$11,"Ambos")+COUNTIFS('Entrega'!$B$6:$B$9,$A48,'Entrega'!$E$6:$E$9,"Diego")+COUNTIFS('Entrega'!$B$6:$B$9,$A48,'Entrega'!$E$6:$E$9,"Ambos")+COUNTIFS('Defensa'!$B$6:$B$10,$A48,'Defensa'!$E$6:$E$10,"Diego")+COUNTIFS('Defensa'!$B$6:$B$10,$A48,'Defensa'!$E$6:$E$10,"Ambos")</f>
         <v/>
       </c>
     </row>
@@ -9956,19 +9977,19 @@
         <v/>
       </c>
       <c r="D49" s="21">
-        <f>SUMIFS('S1'!$I$6:$I$32,'S1'!$B$6:$B$32,$A49,'S1'!$E$6:$E$32,"Víctor")+SUMIFS('S1'!$I$6:$I$32,'S1'!$B$6:$B$32,$A49,'S1'!$E$6:$E$32,"Ambos")+SUMIFS('S2'!$I$6:$I$23,'S2'!$B$6:$B$23,$A49,'S2'!$E$6:$E$23,"Víctor")+SUMIFS('S2'!$I$6:$I$23,'S2'!$B$6:$B$23,$A49,'S2'!$E$6:$E$23,"Ambos")+SUMIFS('S3'!$I$6:$I$19,'S3'!$B$6:$B$19,$A49,'S3'!$E$6:$E$19,"Víctor")+SUMIFS('S3'!$I$6:$I$19,'S3'!$B$6:$B$19,$A49,'S3'!$E$6:$E$19,"Ambos")+SUMIFS('S4'!$I$6:$I$20,'S4'!$B$6:$B$20,$A49,'S4'!$E$6:$E$20,"Víctor")+SUMIFS('S4'!$I$6:$I$20,'S4'!$B$6:$B$20,$A49,'S4'!$E$6:$E$20,"Ambos")+SUMIFS('S5'!$I$6:$I$20,'S5'!$B$6:$B$20,$A49,'S5'!$E$6:$E$20,"Víctor")+SUMIFS('S5'!$I$6:$I$20,'S5'!$B$6:$B$20,$A49,'S5'!$E$6:$E$20,"Ambos")+SUMIFS('S6'!$I$6:$I$17,'S6'!$B$6:$B$17,$A49,'S6'!$E$6:$E$17,"Víctor")+SUMIFS('S6'!$I$6:$I$17,'S6'!$B$6:$B$17,$A49,'S6'!$E$6:$E$17,"Ambos")+SUMIFS('S7'!$I$6:$I$19,'S7'!$B$6:$B$19,$A49,'S7'!$E$6:$E$19,"Víctor")+SUMIFS('S7'!$I$6:$I$19,'S7'!$B$6:$B$19,$A49,'S7'!$E$6:$E$19,"Ambos")+SUMIFS('S8'!$I$6:$I$23,'S8'!$B$6:$B$23,$A49,'S8'!$E$6:$E$23,"Víctor")+SUMIFS('S8'!$I$6:$I$23,'S8'!$B$6:$B$23,$A49,'S8'!$E$6:$E$23,"Ambos")+SUMIFS('S9'!$I$6:$I$15,'S9'!$B$6:$B$15,$A49,'S9'!$E$6:$E$15,"Víctor")+SUMIFS('S9'!$I$6:$I$15,'S9'!$B$6:$B$15,$A49,'S9'!$E$6:$E$15,"Ambos")+SUMIFS('S10'!$I$6:$I$13,'S10'!$B$6:$B$13,$A49,'S10'!$E$6:$E$13,"Víctor")+SUMIFS('S10'!$I$6:$I$13,'S10'!$B$6:$B$13,$A49,'S10'!$E$6:$E$13,"Ambos")+SUMIFS('Holgura'!$I$6:$I$11,'Holgura'!$B$6:$B$11,$A49,'Holgura'!$E$6:$E$11,"Víctor")+SUMIFS('Holgura'!$I$6:$I$11,'Holgura'!$B$6:$B$11,$A49,'Holgura'!$E$6:$E$11,"Ambos")+SUMIFS('Entrega'!$I$6:$I$9,'Entrega'!$B$6:$B$9,$A49,'Entrega'!$E$6:$E$9,"Víctor")+SUMIFS('Entrega'!$I$6:$I$9,'Entrega'!$B$6:$B$9,$A49,'Entrega'!$E$6:$E$9,"Ambos")+SUMIFS('Defensa'!$I$6:$I$10,'Defensa'!$B$6:$B$10,$A49,'Defensa'!$E$6:$E$10,"Víctor")+SUMIFS('Defensa'!$I$6:$I$10,'Defensa'!$B$6:$B$10,$A49,'Defensa'!$E$6:$E$10,"Ambos")</f>
+        <f>SUMIFS('S1'!$I$6:$I$32,'S1'!$B$6:$B$32,$A49,'S1'!$E$6:$E$32,"Víctor")+SUMIFS('S1'!$I$6:$I$32,'S1'!$B$6:$B$32,$A49,'S1'!$E$6:$E$32,"Ambos")+SUMIFS('S2'!$I$6:$I$23,'S2'!$B$6:$B$23,$A49,'S2'!$E$6:$E$23,"Víctor")+SUMIFS('S2'!$I$6:$I$23,'S2'!$B$6:$B$23,$A49,'S2'!$E$6:$E$23,"Ambos")+SUMIFS('S3'!$I$6:$I$24,'S3'!$B$6:$B$24,$A49,'S3'!$E$6:$E$24,"Víctor")+SUMIFS('S3'!$I$6:$I$24,'S3'!$B$6:$B$24,$A49,'S3'!$E$6:$E$24,"Ambos")+SUMIFS('S4'!$I$6:$I$22,'S4'!$B$6:$B$22,$A49,'S4'!$E$6:$E$22,"Víctor")+SUMIFS('S4'!$I$6:$I$22,'S4'!$B$6:$B$22,$A49,'S4'!$E$6:$E$22,"Ambos")+SUMIFS('S5'!$I$6:$I$20,'S5'!$B$6:$B$20,$A49,'S5'!$E$6:$E$20,"Víctor")+SUMIFS('S5'!$I$6:$I$20,'S5'!$B$6:$B$20,$A49,'S5'!$E$6:$E$20,"Ambos")+SUMIFS('S6'!$I$6:$I$17,'S6'!$B$6:$B$17,$A49,'S6'!$E$6:$E$17,"Víctor")+SUMIFS('S6'!$I$6:$I$17,'S6'!$B$6:$B$17,$A49,'S6'!$E$6:$E$17,"Ambos")+SUMIFS('S7'!$I$6:$I$19,'S7'!$B$6:$B$19,$A49,'S7'!$E$6:$E$19,"Víctor")+SUMIFS('S7'!$I$6:$I$19,'S7'!$B$6:$B$19,$A49,'S7'!$E$6:$E$19,"Ambos")+SUMIFS('S8'!$I$6:$I$23,'S8'!$B$6:$B$23,$A49,'S8'!$E$6:$E$23,"Víctor")+SUMIFS('S8'!$I$6:$I$23,'S8'!$B$6:$B$23,$A49,'S8'!$E$6:$E$23,"Ambos")+SUMIFS('S9'!$I$6:$I$15,'S9'!$B$6:$B$15,$A49,'S9'!$E$6:$E$15,"Víctor")+SUMIFS('S9'!$I$6:$I$15,'S9'!$B$6:$B$15,$A49,'S9'!$E$6:$E$15,"Ambos")+SUMIFS('S10'!$I$6:$I$13,'S10'!$B$6:$B$13,$A49,'S10'!$E$6:$E$13,"Víctor")+SUMIFS('S10'!$I$6:$I$13,'S10'!$B$6:$B$13,$A49,'S10'!$E$6:$E$13,"Ambos")+SUMIFS('Holgura'!$I$6:$I$11,'Holgura'!$B$6:$B$11,$A49,'Holgura'!$E$6:$E$11,"Víctor")+SUMIFS('Holgura'!$I$6:$I$11,'Holgura'!$B$6:$B$11,$A49,'Holgura'!$E$6:$E$11,"Ambos")+SUMIFS('Entrega'!$I$6:$I$9,'Entrega'!$B$6:$B$9,$A49,'Entrega'!$E$6:$E$9,"Víctor")+SUMIFS('Entrega'!$I$6:$I$9,'Entrega'!$B$6:$B$9,$A49,'Entrega'!$E$6:$E$9,"Ambos")+SUMIFS('Defensa'!$I$6:$I$10,'Defensa'!$B$6:$B$10,$A49,'Defensa'!$E$6:$E$10,"Víctor")+SUMIFS('Defensa'!$I$6:$I$10,'Defensa'!$B$6:$B$10,$A49,'Defensa'!$E$6:$E$10,"Ambos")</f>
         <v/>
       </c>
       <c r="E49" s="21">
-        <f>SUMIFS('S1'!$I$6:$I$32,'S1'!$B$6:$B$32,$A49,'S1'!$E$6:$E$32,"Diego")+SUMIFS('S1'!$I$6:$I$32,'S1'!$B$6:$B$32,$A49,'S1'!$E$6:$E$32,"Ambos")+SUMIFS('S2'!$I$6:$I$23,'S2'!$B$6:$B$23,$A49,'S2'!$E$6:$E$23,"Diego")+SUMIFS('S2'!$I$6:$I$23,'S2'!$B$6:$B$23,$A49,'S2'!$E$6:$E$23,"Ambos")+SUMIFS('S3'!$I$6:$I$19,'S3'!$B$6:$B$19,$A49,'S3'!$E$6:$E$19,"Diego")+SUMIFS('S3'!$I$6:$I$19,'S3'!$B$6:$B$19,$A49,'S3'!$E$6:$E$19,"Ambos")+SUMIFS('S4'!$I$6:$I$20,'S4'!$B$6:$B$20,$A49,'S4'!$E$6:$E$20,"Diego")+SUMIFS('S4'!$I$6:$I$20,'S4'!$B$6:$B$20,$A49,'S4'!$E$6:$E$20,"Ambos")+SUMIFS('S5'!$I$6:$I$20,'S5'!$B$6:$B$20,$A49,'S5'!$E$6:$E$20,"Diego")+SUMIFS('S5'!$I$6:$I$20,'S5'!$B$6:$B$20,$A49,'S5'!$E$6:$E$20,"Ambos")+SUMIFS('S6'!$I$6:$I$17,'S6'!$B$6:$B$17,$A49,'S6'!$E$6:$E$17,"Diego")+SUMIFS('S6'!$I$6:$I$17,'S6'!$B$6:$B$17,$A49,'S6'!$E$6:$E$17,"Ambos")+SUMIFS('S7'!$I$6:$I$19,'S7'!$B$6:$B$19,$A49,'S7'!$E$6:$E$19,"Diego")+SUMIFS('S7'!$I$6:$I$19,'S7'!$B$6:$B$19,$A49,'S7'!$E$6:$E$19,"Ambos")+SUMIFS('S8'!$I$6:$I$23,'S8'!$B$6:$B$23,$A49,'S8'!$E$6:$E$23,"Diego")+SUMIFS('S8'!$I$6:$I$23,'S8'!$B$6:$B$23,$A49,'S8'!$E$6:$E$23,"Ambos")+SUMIFS('S9'!$I$6:$I$15,'S9'!$B$6:$B$15,$A49,'S9'!$E$6:$E$15,"Diego")+SUMIFS('S9'!$I$6:$I$15,'S9'!$B$6:$B$15,$A49,'S9'!$E$6:$E$15,"Ambos")+SUMIFS('S10'!$I$6:$I$13,'S10'!$B$6:$B$13,$A49,'S10'!$E$6:$E$13,"Diego")+SUMIFS('S10'!$I$6:$I$13,'S10'!$B$6:$B$13,$A49,'S10'!$E$6:$E$13,"Ambos")+SUMIFS('Holgura'!$I$6:$I$11,'Holgura'!$B$6:$B$11,$A49,'Holgura'!$E$6:$E$11,"Diego")+SUMIFS('Holgura'!$I$6:$I$11,'Holgura'!$B$6:$B$11,$A49,'Holgura'!$E$6:$E$11,"Ambos")+SUMIFS('Entrega'!$I$6:$I$9,'Entrega'!$B$6:$B$9,$A49,'Entrega'!$E$6:$E$9,"Diego")+SUMIFS('Entrega'!$I$6:$I$9,'Entrega'!$B$6:$B$9,$A49,'Entrega'!$E$6:$E$9,"Ambos")+SUMIFS('Defensa'!$I$6:$I$10,'Defensa'!$B$6:$B$10,$A49,'Defensa'!$E$6:$E$10,"Diego")+SUMIFS('Defensa'!$I$6:$I$10,'Defensa'!$B$6:$B$10,$A49,'Defensa'!$E$6:$E$10,"Ambos")</f>
+        <f>SUMIFS('S1'!$I$6:$I$32,'S1'!$B$6:$B$32,$A49,'S1'!$E$6:$E$32,"Diego")+SUMIFS('S1'!$I$6:$I$32,'S1'!$B$6:$B$32,$A49,'S1'!$E$6:$E$32,"Ambos")+SUMIFS('S2'!$I$6:$I$23,'S2'!$B$6:$B$23,$A49,'S2'!$E$6:$E$23,"Diego")+SUMIFS('S2'!$I$6:$I$23,'S2'!$B$6:$B$23,$A49,'S2'!$E$6:$E$23,"Ambos")+SUMIFS('S3'!$I$6:$I$24,'S3'!$B$6:$B$24,$A49,'S3'!$E$6:$E$24,"Diego")+SUMIFS('S3'!$I$6:$I$24,'S3'!$B$6:$B$24,$A49,'S3'!$E$6:$E$24,"Ambos")+SUMIFS('S4'!$I$6:$I$22,'S4'!$B$6:$B$22,$A49,'S4'!$E$6:$E$22,"Diego")+SUMIFS('S4'!$I$6:$I$22,'S4'!$B$6:$B$22,$A49,'S4'!$E$6:$E$22,"Ambos")+SUMIFS('S5'!$I$6:$I$20,'S5'!$B$6:$B$20,$A49,'S5'!$E$6:$E$20,"Diego")+SUMIFS('S5'!$I$6:$I$20,'S5'!$B$6:$B$20,$A49,'S5'!$E$6:$E$20,"Ambos")+SUMIFS('S6'!$I$6:$I$17,'S6'!$B$6:$B$17,$A49,'S6'!$E$6:$E$17,"Diego")+SUMIFS('S6'!$I$6:$I$17,'S6'!$B$6:$B$17,$A49,'S6'!$E$6:$E$17,"Ambos")+SUMIFS('S7'!$I$6:$I$19,'S7'!$B$6:$B$19,$A49,'S7'!$E$6:$E$19,"Diego")+SUMIFS('S7'!$I$6:$I$19,'S7'!$B$6:$B$19,$A49,'S7'!$E$6:$E$19,"Ambos")+SUMIFS('S8'!$I$6:$I$23,'S8'!$B$6:$B$23,$A49,'S8'!$E$6:$E$23,"Diego")+SUMIFS('S8'!$I$6:$I$23,'S8'!$B$6:$B$23,$A49,'S8'!$E$6:$E$23,"Ambos")+SUMIFS('S9'!$I$6:$I$15,'S9'!$B$6:$B$15,$A49,'S9'!$E$6:$E$15,"Diego")+SUMIFS('S9'!$I$6:$I$15,'S9'!$B$6:$B$15,$A49,'S9'!$E$6:$E$15,"Ambos")+SUMIFS('S10'!$I$6:$I$13,'S10'!$B$6:$B$13,$A49,'S10'!$E$6:$E$13,"Diego")+SUMIFS('S10'!$I$6:$I$13,'S10'!$B$6:$B$13,$A49,'S10'!$E$6:$E$13,"Ambos")+SUMIFS('Holgura'!$I$6:$I$11,'Holgura'!$B$6:$B$11,$A49,'Holgura'!$E$6:$E$11,"Diego")+SUMIFS('Holgura'!$I$6:$I$11,'Holgura'!$B$6:$B$11,$A49,'Holgura'!$E$6:$E$11,"Ambos")+SUMIFS('Entrega'!$I$6:$I$9,'Entrega'!$B$6:$B$9,$A49,'Entrega'!$E$6:$E$9,"Diego")+SUMIFS('Entrega'!$I$6:$I$9,'Entrega'!$B$6:$B$9,$A49,'Entrega'!$E$6:$E$9,"Ambos")+SUMIFS('Defensa'!$I$6:$I$10,'Defensa'!$B$6:$B$10,$A49,'Defensa'!$E$6:$E$10,"Diego")+SUMIFS('Defensa'!$I$6:$I$10,'Defensa'!$B$6:$B$10,$A49,'Defensa'!$E$6:$E$10,"Ambos")</f>
         <v/>
       </c>
       <c r="F49" s="21">
-        <f>COUNTIFS('S1'!$B$6:$B$32,$A49,'S1'!$E$6:$E$32,"Víctor")+COUNTIFS('S1'!$B$6:$B$32,$A49,'S1'!$E$6:$E$32,"Ambos")+COUNTIFS('S2'!$B$6:$B$23,$A49,'S2'!$E$6:$E$23,"Víctor")+COUNTIFS('S2'!$B$6:$B$23,$A49,'S2'!$E$6:$E$23,"Ambos")+COUNTIFS('S3'!$B$6:$B$19,$A49,'S3'!$E$6:$E$19,"Víctor")+COUNTIFS('S3'!$B$6:$B$19,$A49,'S3'!$E$6:$E$19,"Ambos")+COUNTIFS('S4'!$B$6:$B$20,$A49,'S4'!$E$6:$E$20,"Víctor")+COUNTIFS('S4'!$B$6:$B$20,$A49,'S4'!$E$6:$E$20,"Ambos")+COUNTIFS('S5'!$B$6:$B$20,$A49,'S5'!$E$6:$E$20,"Víctor")+COUNTIFS('S5'!$B$6:$B$20,$A49,'S5'!$E$6:$E$20,"Ambos")+COUNTIFS('S6'!$B$6:$B$17,$A49,'S6'!$E$6:$E$17,"Víctor")+COUNTIFS('S6'!$B$6:$B$17,$A49,'S6'!$E$6:$E$17,"Ambos")+COUNTIFS('S7'!$B$6:$B$19,$A49,'S7'!$E$6:$E$19,"Víctor")+COUNTIFS('S7'!$B$6:$B$19,$A49,'S7'!$E$6:$E$19,"Ambos")+COUNTIFS('S8'!$B$6:$B$23,$A49,'S8'!$E$6:$E$23,"Víctor")+COUNTIFS('S8'!$B$6:$B$23,$A49,'S8'!$E$6:$E$23,"Ambos")+COUNTIFS('S9'!$B$6:$B$15,$A49,'S9'!$E$6:$E$15,"Víctor")+COUNTIFS('S9'!$B$6:$B$15,$A49,'S9'!$E$6:$E$15,"Ambos")+COUNTIFS('S10'!$B$6:$B$13,$A49,'S10'!$E$6:$E$13,"Víctor")+COUNTIFS('S10'!$B$6:$B$13,$A49,'S10'!$E$6:$E$13,"Ambos")+COUNTIFS('Holgura'!$B$6:$B$11,$A49,'Holgura'!$E$6:$E$11,"Víctor")+COUNTIFS('Holgura'!$B$6:$B$11,$A49,'Holgura'!$E$6:$E$11,"Ambos")+COUNTIFS('Entrega'!$B$6:$B$9,$A49,'Entrega'!$E$6:$E$9,"Víctor")+COUNTIFS('Entrega'!$B$6:$B$9,$A49,'Entrega'!$E$6:$E$9,"Ambos")+COUNTIFS('Defensa'!$B$6:$B$10,$A49,'Defensa'!$E$6:$E$10,"Víctor")+COUNTIFS('Defensa'!$B$6:$B$10,$A49,'Defensa'!$E$6:$E$10,"Ambos")</f>
+        <f>COUNTIFS('S1'!$B$6:$B$32,$A49,'S1'!$E$6:$E$32,"Víctor")+COUNTIFS('S1'!$B$6:$B$32,$A49,'S1'!$E$6:$E$32,"Ambos")+COUNTIFS('S2'!$B$6:$B$23,$A49,'S2'!$E$6:$E$23,"Víctor")+COUNTIFS('S2'!$B$6:$B$23,$A49,'S2'!$E$6:$E$23,"Ambos")+COUNTIFS('S3'!$B$6:$B$24,$A49,'S3'!$E$6:$E$24,"Víctor")+COUNTIFS('S3'!$B$6:$B$24,$A49,'S3'!$E$6:$E$24,"Ambos")+COUNTIFS('S4'!$B$6:$B$22,$A49,'S4'!$E$6:$E$22,"Víctor")+COUNTIFS('S4'!$B$6:$B$22,$A49,'S4'!$E$6:$E$22,"Ambos")+COUNTIFS('S5'!$B$6:$B$20,$A49,'S5'!$E$6:$E$20,"Víctor")+COUNTIFS('S5'!$B$6:$B$20,$A49,'S5'!$E$6:$E$20,"Ambos")+COUNTIFS('S6'!$B$6:$B$17,$A49,'S6'!$E$6:$E$17,"Víctor")+COUNTIFS('S6'!$B$6:$B$17,$A49,'S6'!$E$6:$E$17,"Ambos")+COUNTIFS('S7'!$B$6:$B$19,$A49,'S7'!$E$6:$E$19,"Víctor")+COUNTIFS('S7'!$B$6:$B$19,$A49,'S7'!$E$6:$E$19,"Ambos")+COUNTIFS('S8'!$B$6:$B$23,$A49,'S8'!$E$6:$E$23,"Víctor")+COUNTIFS('S8'!$B$6:$B$23,$A49,'S8'!$E$6:$E$23,"Ambos")+COUNTIFS('S9'!$B$6:$B$15,$A49,'S9'!$E$6:$E$15,"Víctor")+COUNTIFS('S9'!$B$6:$B$15,$A49,'S9'!$E$6:$E$15,"Ambos")+COUNTIFS('S10'!$B$6:$B$13,$A49,'S10'!$E$6:$E$13,"Víctor")+COUNTIFS('S10'!$B$6:$B$13,$A49,'S10'!$E$6:$E$13,"Ambos")+COUNTIFS('Holgura'!$B$6:$B$11,$A49,'Holgura'!$E$6:$E$11,"Víctor")+COUNTIFS('Holgura'!$B$6:$B$11,$A49,'Holgura'!$E$6:$E$11,"Ambos")+COUNTIFS('Entrega'!$B$6:$B$9,$A49,'Entrega'!$E$6:$E$9,"Víctor")+COUNTIFS('Entrega'!$B$6:$B$9,$A49,'Entrega'!$E$6:$E$9,"Ambos")+COUNTIFS('Defensa'!$B$6:$B$10,$A49,'Defensa'!$E$6:$E$10,"Víctor")+COUNTIFS('Defensa'!$B$6:$B$10,$A49,'Defensa'!$E$6:$E$10,"Ambos")</f>
         <v/>
       </c>
       <c r="G49" s="21">
-        <f>COUNTIFS('S1'!$B$6:$B$32,$A49,'S1'!$E$6:$E$32,"Diego")+COUNTIFS('S1'!$B$6:$B$32,$A49,'S1'!$E$6:$E$32,"Ambos")+COUNTIFS('S2'!$B$6:$B$23,$A49,'S2'!$E$6:$E$23,"Diego")+COUNTIFS('S2'!$B$6:$B$23,$A49,'S2'!$E$6:$E$23,"Ambos")+COUNTIFS('S3'!$B$6:$B$19,$A49,'S3'!$E$6:$E$19,"Diego")+COUNTIFS('S3'!$B$6:$B$19,$A49,'S3'!$E$6:$E$19,"Ambos")+COUNTIFS('S4'!$B$6:$B$20,$A49,'S4'!$E$6:$E$20,"Diego")+COUNTIFS('S4'!$B$6:$B$20,$A49,'S4'!$E$6:$E$20,"Ambos")+COUNTIFS('S5'!$B$6:$B$20,$A49,'S5'!$E$6:$E$20,"Diego")+COUNTIFS('S5'!$B$6:$B$20,$A49,'S5'!$E$6:$E$20,"Ambos")+COUNTIFS('S6'!$B$6:$B$17,$A49,'S6'!$E$6:$E$17,"Diego")+COUNTIFS('S6'!$B$6:$B$17,$A49,'S6'!$E$6:$E$17,"Ambos")+COUNTIFS('S7'!$B$6:$B$19,$A49,'S7'!$E$6:$E$19,"Diego")+COUNTIFS('S7'!$B$6:$B$19,$A49,'S7'!$E$6:$E$19,"Ambos")+COUNTIFS('S8'!$B$6:$B$23,$A49,'S8'!$E$6:$E$23,"Diego")+COUNTIFS('S8'!$B$6:$B$23,$A49,'S8'!$E$6:$E$23,"Ambos")+COUNTIFS('S9'!$B$6:$B$15,$A49,'S9'!$E$6:$E$15,"Diego")+COUNTIFS('S9'!$B$6:$B$15,$A49,'S9'!$E$6:$E$15,"Ambos")+COUNTIFS('S10'!$B$6:$B$13,$A49,'S10'!$E$6:$E$13,"Diego")+COUNTIFS('S10'!$B$6:$B$13,$A49,'S10'!$E$6:$E$13,"Ambos")+COUNTIFS('Holgura'!$B$6:$B$11,$A49,'Holgura'!$E$6:$E$11,"Diego")+COUNTIFS('Holgura'!$B$6:$B$11,$A49,'Holgura'!$E$6:$E$11,"Ambos")+COUNTIFS('Entrega'!$B$6:$B$9,$A49,'Entrega'!$E$6:$E$9,"Diego")+COUNTIFS('Entrega'!$B$6:$B$9,$A49,'Entrega'!$E$6:$E$9,"Ambos")+COUNTIFS('Defensa'!$B$6:$B$10,$A49,'Defensa'!$E$6:$E$10,"Diego")+COUNTIFS('Defensa'!$B$6:$B$10,$A49,'Defensa'!$E$6:$E$10,"Ambos")</f>
+        <f>COUNTIFS('S1'!$B$6:$B$32,$A49,'S1'!$E$6:$E$32,"Diego")+COUNTIFS('S1'!$B$6:$B$32,$A49,'S1'!$E$6:$E$32,"Ambos")+COUNTIFS('S2'!$B$6:$B$23,$A49,'S2'!$E$6:$E$23,"Diego")+COUNTIFS('S2'!$B$6:$B$23,$A49,'S2'!$E$6:$E$23,"Ambos")+COUNTIFS('S3'!$B$6:$B$24,$A49,'S3'!$E$6:$E$24,"Diego")+COUNTIFS('S3'!$B$6:$B$24,$A49,'S3'!$E$6:$E$24,"Ambos")+COUNTIFS('S4'!$B$6:$B$22,$A49,'S4'!$E$6:$E$22,"Diego")+COUNTIFS('S4'!$B$6:$B$22,$A49,'S4'!$E$6:$E$22,"Ambos")+COUNTIFS('S5'!$B$6:$B$20,$A49,'S5'!$E$6:$E$20,"Diego")+COUNTIFS('S5'!$B$6:$B$20,$A49,'S5'!$E$6:$E$20,"Ambos")+COUNTIFS('S6'!$B$6:$B$17,$A49,'S6'!$E$6:$E$17,"Diego")+COUNTIFS('S6'!$B$6:$B$17,$A49,'S6'!$E$6:$E$17,"Ambos")+COUNTIFS('S7'!$B$6:$B$19,$A49,'S7'!$E$6:$E$19,"Diego")+COUNTIFS('S7'!$B$6:$B$19,$A49,'S7'!$E$6:$E$19,"Ambos")+COUNTIFS('S8'!$B$6:$B$23,$A49,'S8'!$E$6:$E$23,"Diego")+COUNTIFS('S8'!$B$6:$B$23,$A49,'S8'!$E$6:$E$23,"Ambos")+COUNTIFS('S9'!$B$6:$B$15,$A49,'S9'!$E$6:$E$15,"Diego")+COUNTIFS('S9'!$B$6:$B$15,$A49,'S9'!$E$6:$E$15,"Ambos")+COUNTIFS('S10'!$B$6:$B$13,$A49,'S10'!$E$6:$E$13,"Diego")+COUNTIFS('S10'!$B$6:$B$13,$A49,'S10'!$E$6:$E$13,"Ambos")+COUNTIFS('Holgura'!$B$6:$B$11,$A49,'Holgura'!$E$6:$E$11,"Diego")+COUNTIFS('Holgura'!$B$6:$B$11,$A49,'Holgura'!$E$6:$E$11,"Ambos")+COUNTIFS('Entrega'!$B$6:$B$9,$A49,'Entrega'!$E$6:$E$9,"Diego")+COUNTIFS('Entrega'!$B$6:$B$9,$A49,'Entrega'!$E$6:$E$9,"Ambos")+COUNTIFS('Defensa'!$B$6:$B$10,$A49,'Defensa'!$E$6:$E$10,"Diego")+COUNTIFS('Defensa'!$B$6:$B$10,$A49,'Defensa'!$E$6:$E$10,"Ambos")</f>
         <v/>
       </c>
     </row>
@@ -9985,19 +10006,19 @@
         <v/>
       </c>
       <c r="D50" s="21">
-        <f>SUMIFS('S1'!$I$6:$I$32,'S1'!$B$6:$B$32,$A50,'S1'!$E$6:$E$32,"Víctor")+SUMIFS('S1'!$I$6:$I$32,'S1'!$B$6:$B$32,$A50,'S1'!$E$6:$E$32,"Ambos")+SUMIFS('S2'!$I$6:$I$23,'S2'!$B$6:$B$23,$A50,'S2'!$E$6:$E$23,"Víctor")+SUMIFS('S2'!$I$6:$I$23,'S2'!$B$6:$B$23,$A50,'S2'!$E$6:$E$23,"Ambos")+SUMIFS('S3'!$I$6:$I$19,'S3'!$B$6:$B$19,$A50,'S3'!$E$6:$E$19,"Víctor")+SUMIFS('S3'!$I$6:$I$19,'S3'!$B$6:$B$19,$A50,'S3'!$E$6:$E$19,"Ambos")+SUMIFS('S4'!$I$6:$I$20,'S4'!$B$6:$B$20,$A50,'S4'!$E$6:$E$20,"Víctor")+SUMIFS('S4'!$I$6:$I$20,'S4'!$B$6:$B$20,$A50,'S4'!$E$6:$E$20,"Ambos")+SUMIFS('S5'!$I$6:$I$20,'S5'!$B$6:$B$20,$A50,'S5'!$E$6:$E$20,"Víctor")+SUMIFS('S5'!$I$6:$I$20,'S5'!$B$6:$B$20,$A50,'S5'!$E$6:$E$20,"Ambos")+SUMIFS('S6'!$I$6:$I$17,'S6'!$B$6:$B$17,$A50,'S6'!$E$6:$E$17,"Víctor")+SUMIFS('S6'!$I$6:$I$17,'S6'!$B$6:$B$17,$A50,'S6'!$E$6:$E$17,"Ambos")+SUMIFS('S7'!$I$6:$I$19,'S7'!$B$6:$B$19,$A50,'S7'!$E$6:$E$19,"Víctor")+SUMIFS('S7'!$I$6:$I$19,'S7'!$B$6:$B$19,$A50,'S7'!$E$6:$E$19,"Ambos")+SUMIFS('S8'!$I$6:$I$23,'S8'!$B$6:$B$23,$A50,'S8'!$E$6:$E$23,"Víctor")+SUMIFS('S8'!$I$6:$I$23,'S8'!$B$6:$B$23,$A50,'S8'!$E$6:$E$23,"Ambos")+SUMIFS('S9'!$I$6:$I$15,'S9'!$B$6:$B$15,$A50,'S9'!$E$6:$E$15,"Víctor")+SUMIFS('S9'!$I$6:$I$15,'S9'!$B$6:$B$15,$A50,'S9'!$E$6:$E$15,"Ambos")+SUMIFS('S10'!$I$6:$I$13,'S10'!$B$6:$B$13,$A50,'S10'!$E$6:$E$13,"Víctor")+SUMIFS('S10'!$I$6:$I$13,'S10'!$B$6:$B$13,$A50,'S10'!$E$6:$E$13,"Ambos")+SUMIFS('Holgura'!$I$6:$I$11,'Holgura'!$B$6:$B$11,$A50,'Holgura'!$E$6:$E$11,"Víctor")+SUMIFS('Holgura'!$I$6:$I$11,'Holgura'!$B$6:$B$11,$A50,'Holgura'!$E$6:$E$11,"Ambos")+SUMIFS('Entrega'!$I$6:$I$9,'Entrega'!$B$6:$B$9,$A50,'Entrega'!$E$6:$E$9,"Víctor")+SUMIFS('Entrega'!$I$6:$I$9,'Entrega'!$B$6:$B$9,$A50,'Entrega'!$E$6:$E$9,"Ambos")+SUMIFS('Defensa'!$I$6:$I$10,'Defensa'!$B$6:$B$10,$A50,'Defensa'!$E$6:$E$10,"Víctor")+SUMIFS('Defensa'!$I$6:$I$10,'Defensa'!$B$6:$B$10,$A50,'Defensa'!$E$6:$E$10,"Ambos")</f>
+        <f>SUMIFS('S1'!$I$6:$I$32,'S1'!$B$6:$B$32,$A50,'S1'!$E$6:$E$32,"Víctor")+SUMIFS('S1'!$I$6:$I$32,'S1'!$B$6:$B$32,$A50,'S1'!$E$6:$E$32,"Ambos")+SUMIFS('S2'!$I$6:$I$23,'S2'!$B$6:$B$23,$A50,'S2'!$E$6:$E$23,"Víctor")+SUMIFS('S2'!$I$6:$I$23,'S2'!$B$6:$B$23,$A50,'S2'!$E$6:$E$23,"Ambos")+SUMIFS('S3'!$I$6:$I$24,'S3'!$B$6:$B$24,$A50,'S3'!$E$6:$E$24,"Víctor")+SUMIFS('S3'!$I$6:$I$24,'S3'!$B$6:$B$24,$A50,'S3'!$E$6:$E$24,"Ambos")+SUMIFS('S4'!$I$6:$I$22,'S4'!$B$6:$B$22,$A50,'S4'!$E$6:$E$22,"Víctor")+SUMIFS('S4'!$I$6:$I$22,'S4'!$B$6:$B$22,$A50,'S4'!$E$6:$E$22,"Ambos")+SUMIFS('S5'!$I$6:$I$20,'S5'!$B$6:$B$20,$A50,'S5'!$E$6:$E$20,"Víctor")+SUMIFS('S5'!$I$6:$I$20,'S5'!$B$6:$B$20,$A50,'S5'!$E$6:$E$20,"Ambos")+SUMIFS('S6'!$I$6:$I$17,'S6'!$B$6:$B$17,$A50,'S6'!$E$6:$E$17,"Víctor")+SUMIFS('S6'!$I$6:$I$17,'S6'!$B$6:$B$17,$A50,'S6'!$E$6:$E$17,"Ambos")+SUMIFS('S7'!$I$6:$I$19,'S7'!$B$6:$B$19,$A50,'S7'!$E$6:$E$19,"Víctor")+SUMIFS('S7'!$I$6:$I$19,'S7'!$B$6:$B$19,$A50,'S7'!$E$6:$E$19,"Ambos")+SUMIFS('S8'!$I$6:$I$23,'S8'!$B$6:$B$23,$A50,'S8'!$E$6:$E$23,"Víctor")+SUMIFS('S8'!$I$6:$I$23,'S8'!$B$6:$B$23,$A50,'S8'!$E$6:$E$23,"Ambos")+SUMIFS('S9'!$I$6:$I$15,'S9'!$B$6:$B$15,$A50,'S9'!$E$6:$E$15,"Víctor")+SUMIFS('S9'!$I$6:$I$15,'S9'!$B$6:$B$15,$A50,'S9'!$E$6:$E$15,"Ambos")+SUMIFS('S10'!$I$6:$I$13,'S10'!$B$6:$B$13,$A50,'S10'!$E$6:$E$13,"Víctor")+SUMIFS('S10'!$I$6:$I$13,'S10'!$B$6:$B$13,$A50,'S10'!$E$6:$E$13,"Ambos")+SUMIFS('Holgura'!$I$6:$I$11,'Holgura'!$B$6:$B$11,$A50,'Holgura'!$E$6:$E$11,"Víctor")+SUMIFS('Holgura'!$I$6:$I$11,'Holgura'!$B$6:$B$11,$A50,'Holgura'!$E$6:$E$11,"Ambos")+SUMIFS('Entrega'!$I$6:$I$9,'Entrega'!$B$6:$B$9,$A50,'Entrega'!$E$6:$E$9,"Víctor")+SUMIFS('Entrega'!$I$6:$I$9,'Entrega'!$B$6:$B$9,$A50,'Entrega'!$E$6:$E$9,"Ambos")+SUMIFS('Defensa'!$I$6:$I$10,'Defensa'!$B$6:$B$10,$A50,'Defensa'!$E$6:$E$10,"Víctor")+SUMIFS('Defensa'!$I$6:$I$10,'Defensa'!$B$6:$B$10,$A50,'Defensa'!$E$6:$E$10,"Ambos")</f>
         <v/>
       </c>
       <c r="E50" s="21">
-        <f>SUMIFS('S1'!$I$6:$I$32,'S1'!$B$6:$B$32,$A50,'S1'!$E$6:$E$32,"Diego")+SUMIFS('S1'!$I$6:$I$32,'S1'!$B$6:$B$32,$A50,'S1'!$E$6:$E$32,"Ambos")+SUMIFS('S2'!$I$6:$I$23,'S2'!$B$6:$B$23,$A50,'S2'!$E$6:$E$23,"Diego")+SUMIFS('S2'!$I$6:$I$23,'S2'!$B$6:$B$23,$A50,'S2'!$E$6:$E$23,"Ambos")+SUMIFS('S3'!$I$6:$I$19,'S3'!$B$6:$B$19,$A50,'S3'!$E$6:$E$19,"Diego")+SUMIFS('S3'!$I$6:$I$19,'S3'!$B$6:$B$19,$A50,'S3'!$E$6:$E$19,"Ambos")+SUMIFS('S4'!$I$6:$I$20,'S4'!$B$6:$B$20,$A50,'S4'!$E$6:$E$20,"Diego")+SUMIFS('S4'!$I$6:$I$20,'S4'!$B$6:$B$20,$A50,'S4'!$E$6:$E$20,"Ambos")+SUMIFS('S5'!$I$6:$I$20,'S5'!$B$6:$B$20,$A50,'S5'!$E$6:$E$20,"Diego")+SUMIFS('S5'!$I$6:$I$20,'S5'!$B$6:$B$20,$A50,'S5'!$E$6:$E$20,"Ambos")+SUMIFS('S6'!$I$6:$I$17,'S6'!$B$6:$B$17,$A50,'S6'!$E$6:$E$17,"Diego")+SUMIFS('S6'!$I$6:$I$17,'S6'!$B$6:$B$17,$A50,'S6'!$E$6:$E$17,"Ambos")+SUMIFS('S7'!$I$6:$I$19,'S7'!$B$6:$B$19,$A50,'S7'!$E$6:$E$19,"Diego")+SUMIFS('S7'!$I$6:$I$19,'S7'!$B$6:$B$19,$A50,'S7'!$E$6:$E$19,"Ambos")+SUMIFS('S8'!$I$6:$I$23,'S8'!$B$6:$B$23,$A50,'S8'!$E$6:$E$23,"Diego")+SUMIFS('S8'!$I$6:$I$23,'S8'!$B$6:$B$23,$A50,'S8'!$E$6:$E$23,"Ambos")+SUMIFS('S9'!$I$6:$I$15,'S9'!$B$6:$B$15,$A50,'S9'!$E$6:$E$15,"Diego")+SUMIFS('S9'!$I$6:$I$15,'S9'!$B$6:$B$15,$A50,'S9'!$E$6:$E$15,"Ambos")+SUMIFS('S10'!$I$6:$I$13,'S10'!$B$6:$B$13,$A50,'S10'!$E$6:$E$13,"Diego")+SUMIFS('S10'!$I$6:$I$13,'S10'!$B$6:$B$13,$A50,'S10'!$E$6:$E$13,"Ambos")+SUMIFS('Holgura'!$I$6:$I$11,'Holgura'!$B$6:$B$11,$A50,'Holgura'!$E$6:$E$11,"Diego")+SUMIFS('Holgura'!$I$6:$I$11,'Holgura'!$B$6:$B$11,$A50,'Holgura'!$E$6:$E$11,"Ambos")+SUMIFS('Entrega'!$I$6:$I$9,'Entrega'!$B$6:$B$9,$A50,'Entrega'!$E$6:$E$9,"Diego")+SUMIFS('Entrega'!$I$6:$I$9,'Entrega'!$B$6:$B$9,$A50,'Entrega'!$E$6:$E$9,"Ambos")+SUMIFS('Defensa'!$I$6:$I$10,'Defensa'!$B$6:$B$10,$A50,'Defensa'!$E$6:$E$10,"Diego")+SUMIFS('Defensa'!$I$6:$I$10,'Defensa'!$B$6:$B$10,$A50,'Defensa'!$E$6:$E$10,"Ambos")</f>
+        <f>SUMIFS('S1'!$I$6:$I$32,'S1'!$B$6:$B$32,$A50,'S1'!$E$6:$E$32,"Diego")+SUMIFS('S1'!$I$6:$I$32,'S1'!$B$6:$B$32,$A50,'S1'!$E$6:$E$32,"Ambos")+SUMIFS('S2'!$I$6:$I$23,'S2'!$B$6:$B$23,$A50,'S2'!$E$6:$E$23,"Diego")+SUMIFS('S2'!$I$6:$I$23,'S2'!$B$6:$B$23,$A50,'S2'!$E$6:$E$23,"Ambos")+SUMIFS('S3'!$I$6:$I$24,'S3'!$B$6:$B$24,$A50,'S3'!$E$6:$E$24,"Diego")+SUMIFS('S3'!$I$6:$I$24,'S3'!$B$6:$B$24,$A50,'S3'!$E$6:$E$24,"Ambos")+SUMIFS('S4'!$I$6:$I$22,'S4'!$B$6:$B$22,$A50,'S4'!$E$6:$E$22,"Diego")+SUMIFS('S4'!$I$6:$I$22,'S4'!$B$6:$B$22,$A50,'S4'!$E$6:$E$22,"Ambos")+SUMIFS('S5'!$I$6:$I$20,'S5'!$B$6:$B$20,$A50,'S5'!$E$6:$E$20,"Diego")+SUMIFS('S5'!$I$6:$I$20,'S5'!$B$6:$B$20,$A50,'S5'!$E$6:$E$20,"Ambos")+SUMIFS('S6'!$I$6:$I$17,'S6'!$B$6:$B$17,$A50,'S6'!$E$6:$E$17,"Diego")+SUMIFS('S6'!$I$6:$I$17,'S6'!$B$6:$B$17,$A50,'S6'!$E$6:$E$17,"Ambos")+SUMIFS('S7'!$I$6:$I$19,'S7'!$B$6:$B$19,$A50,'S7'!$E$6:$E$19,"Diego")+SUMIFS('S7'!$I$6:$I$19,'S7'!$B$6:$B$19,$A50,'S7'!$E$6:$E$19,"Ambos")+SUMIFS('S8'!$I$6:$I$23,'S8'!$B$6:$B$23,$A50,'S8'!$E$6:$E$23,"Diego")+SUMIFS('S8'!$I$6:$I$23,'S8'!$B$6:$B$23,$A50,'S8'!$E$6:$E$23,"Ambos")+SUMIFS('S9'!$I$6:$I$15,'S9'!$B$6:$B$15,$A50,'S9'!$E$6:$E$15,"Diego")+SUMIFS('S9'!$I$6:$I$15,'S9'!$B$6:$B$15,$A50,'S9'!$E$6:$E$15,"Ambos")+SUMIFS('S10'!$I$6:$I$13,'S10'!$B$6:$B$13,$A50,'S10'!$E$6:$E$13,"Diego")+SUMIFS('S10'!$I$6:$I$13,'S10'!$B$6:$B$13,$A50,'S10'!$E$6:$E$13,"Ambos")+SUMIFS('Holgura'!$I$6:$I$11,'Holgura'!$B$6:$B$11,$A50,'Holgura'!$E$6:$E$11,"Diego")+SUMIFS('Holgura'!$I$6:$I$11,'Holgura'!$B$6:$B$11,$A50,'Holgura'!$E$6:$E$11,"Ambos")+SUMIFS('Entrega'!$I$6:$I$9,'Entrega'!$B$6:$B$9,$A50,'Entrega'!$E$6:$E$9,"Diego")+SUMIFS('Entrega'!$I$6:$I$9,'Entrega'!$B$6:$B$9,$A50,'Entrega'!$E$6:$E$9,"Ambos")+SUMIFS('Defensa'!$I$6:$I$10,'Defensa'!$B$6:$B$10,$A50,'Defensa'!$E$6:$E$10,"Diego")+SUMIFS('Defensa'!$I$6:$I$10,'Defensa'!$B$6:$B$10,$A50,'Defensa'!$E$6:$E$10,"Ambos")</f>
         <v/>
       </c>
       <c r="F50" s="21">
-        <f>COUNTIFS('S1'!$B$6:$B$32,$A50,'S1'!$E$6:$E$32,"Víctor")+COUNTIFS('S1'!$B$6:$B$32,$A50,'S1'!$E$6:$E$32,"Ambos")+COUNTIFS('S2'!$B$6:$B$23,$A50,'S2'!$E$6:$E$23,"Víctor")+COUNTIFS('S2'!$B$6:$B$23,$A50,'S2'!$E$6:$E$23,"Ambos")+COUNTIFS('S3'!$B$6:$B$19,$A50,'S3'!$E$6:$E$19,"Víctor")+COUNTIFS('S3'!$B$6:$B$19,$A50,'S3'!$E$6:$E$19,"Ambos")+COUNTIFS('S4'!$B$6:$B$20,$A50,'S4'!$E$6:$E$20,"Víctor")+COUNTIFS('S4'!$B$6:$B$20,$A50,'S4'!$E$6:$E$20,"Ambos")+COUNTIFS('S5'!$B$6:$B$20,$A50,'S5'!$E$6:$E$20,"Víctor")+COUNTIFS('S5'!$B$6:$B$20,$A50,'S5'!$E$6:$E$20,"Ambos")+COUNTIFS('S6'!$B$6:$B$17,$A50,'S6'!$E$6:$E$17,"Víctor")+COUNTIFS('S6'!$B$6:$B$17,$A50,'S6'!$E$6:$E$17,"Ambos")+COUNTIFS('S7'!$B$6:$B$19,$A50,'S7'!$E$6:$E$19,"Víctor")+COUNTIFS('S7'!$B$6:$B$19,$A50,'S7'!$E$6:$E$19,"Ambos")+COUNTIFS('S8'!$B$6:$B$23,$A50,'S8'!$E$6:$E$23,"Víctor")+COUNTIFS('S8'!$B$6:$B$23,$A50,'S8'!$E$6:$E$23,"Ambos")+COUNTIFS('S9'!$B$6:$B$15,$A50,'S9'!$E$6:$E$15,"Víctor")+COUNTIFS('S9'!$B$6:$B$15,$A50,'S9'!$E$6:$E$15,"Ambos")+COUNTIFS('S10'!$B$6:$B$13,$A50,'S10'!$E$6:$E$13,"Víctor")+COUNTIFS('S10'!$B$6:$B$13,$A50,'S10'!$E$6:$E$13,"Ambos")+COUNTIFS('Holgura'!$B$6:$B$11,$A50,'Holgura'!$E$6:$E$11,"Víctor")+COUNTIFS('Holgura'!$B$6:$B$11,$A50,'Holgura'!$E$6:$E$11,"Ambos")+COUNTIFS('Entrega'!$B$6:$B$9,$A50,'Entrega'!$E$6:$E$9,"Víctor")+COUNTIFS('Entrega'!$B$6:$B$9,$A50,'Entrega'!$E$6:$E$9,"Ambos")+COUNTIFS('Defensa'!$B$6:$B$10,$A50,'Defensa'!$E$6:$E$10,"Víctor")+COUNTIFS('Defensa'!$B$6:$B$10,$A50,'Defensa'!$E$6:$E$10,"Ambos")</f>
+        <f>COUNTIFS('S1'!$B$6:$B$32,$A50,'S1'!$E$6:$E$32,"Víctor")+COUNTIFS('S1'!$B$6:$B$32,$A50,'S1'!$E$6:$E$32,"Ambos")+COUNTIFS('S2'!$B$6:$B$23,$A50,'S2'!$E$6:$E$23,"Víctor")+COUNTIFS('S2'!$B$6:$B$23,$A50,'S2'!$E$6:$E$23,"Ambos")+COUNTIFS('S3'!$B$6:$B$24,$A50,'S3'!$E$6:$E$24,"Víctor")+COUNTIFS('S3'!$B$6:$B$24,$A50,'S3'!$E$6:$E$24,"Ambos")+COUNTIFS('S4'!$B$6:$B$22,$A50,'S4'!$E$6:$E$22,"Víctor")+COUNTIFS('S4'!$B$6:$B$22,$A50,'S4'!$E$6:$E$22,"Ambos")+COUNTIFS('S5'!$B$6:$B$20,$A50,'S5'!$E$6:$E$20,"Víctor")+COUNTIFS('S5'!$B$6:$B$20,$A50,'S5'!$E$6:$E$20,"Ambos")+COUNTIFS('S6'!$B$6:$B$17,$A50,'S6'!$E$6:$E$17,"Víctor")+COUNTIFS('S6'!$B$6:$B$17,$A50,'S6'!$E$6:$E$17,"Ambos")+COUNTIFS('S7'!$B$6:$B$19,$A50,'S7'!$E$6:$E$19,"Víctor")+COUNTIFS('S7'!$B$6:$B$19,$A50,'S7'!$E$6:$E$19,"Ambos")+COUNTIFS('S8'!$B$6:$B$23,$A50,'S8'!$E$6:$E$23,"Víctor")+COUNTIFS('S8'!$B$6:$B$23,$A50,'S8'!$E$6:$E$23,"Ambos")+COUNTIFS('S9'!$B$6:$B$15,$A50,'S9'!$E$6:$E$15,"Víctor")+COUNTIFS('S9'!$B$6:$B$15,$A50,'S9'!$E$6:$E$15,"Ambos")+COUNTIFS('S10'!$B$6:$B$13,$A50,'S10'!$E$6:$E$13,"Víctor")+COUNTIFS('S10'!$B$6:$B$13,$A50,'S10'!$E$6:$E$13,"Ambos")+COUNTIFS('Holgura'!$B$6:$B$11,$A50,'Holgura'!$E$6:$E$11,"Víctor")+COUNTIFS('Holgura'!$B$6:$B$11,$A50,'Holgura'!$E$6:$E$11,"Ambos")+COUNTIFS('Entrega'!$B$6:$B$9,$A50,'Entrega'!$E$6:$E$9,"Víctor")+COUNTIFS('Entrega'!$B$6:$B$9,$A50,'Entrega'!$E$6:$E$9,"Ambos")+COUNTIFS('Defensa'!$B$6:$B$10,$A50,'Defensa'!$E$6:$E$10,"Víctor")+COUNTIFS('Defensa'!$B$6:$B$10,$A50,'Defensa'!$E$6:$E$10,"Ambos")</f>
         <v/>
       </c>
       <c r="G50" s="21">
-        <f>COUNTIFS('S1'!$B$6:$B$32,$A50,'S1'!$E$6:$E$32,"Diego")+COUNTIFS('S1'!$B$6:$B$32,$A50,'S1'!$E$6:$E$32,"Ambos")+COUNTIFS('S2'!$B$6:$B$23,$A50,'S2'!$E$6:$E$23,"Diego")+COUNTIFS('S2'!$B$6:$B$23,$A50,'S2'!$E$6:$E$23,"Ambos")+COUNTIFS('S3'!$B$6:$B$19,$A50,'S3'!$E$6:$E$19,"Diego")+COUNTIFS('S3'!$B$6:$B$19,$A50,'S3'!$E$6:$E$19,"Ambos")+COUNTIFS('S4'!$B$6:$B$20,$A50,'S4'!$E$6:$E$20,"Diego")+COUNTIFS('S4'!$B$6:$B$20,$A50,'S4'!$E$6:$E$20,"Ambos")+COUNTIFS('S5'!$B$6:$B$20,$A50,'S5'!$E$6:$E$20,"Diego")+COUNTIFS('S5'!$B$6:$B$20,$A50,'S5'!$E$6:$E$20,"Ambos")+COUNTIFS('S6'!$B$6:$B$17,$A50,'S6'!$E$6:$E$17,"Diego")+COUNTIFS('S6'!$B$6:$B$17,$A50,'S6'!$E$6:$E$17,"Ambos")+COUNTIFS('S7'!$B$6:$B$19,$A50,'S7'!$E$6:$E$19,"Diego")+COUNTIFS('S7'!$B$6:$B$19,$A50,'S7'!$E$6:$E$19,"Ambos")+COUNTIFS('S8'!$B$6:$B$23,$A50,'S8'!$E$6:$E$23,"Diego")+COUNTIFS('S8'!$B$6:$B$23,$A50,'S8'!$E$6:$E$23,"Ambos")+COUNTIFS('S9'!$B$6:$B$15,$A50,'S9'!$E$6:$E$15,"Diego")+COUNTIFS('S9'!$B$6:$B$15,$A50,'S9'!$E$6:$E$15,"Ambos")+COUNTIFS('S10'!$B$6:$B$13,$A50,'S10'!$E$6:$E$13,"Diego")+COUNTIFS('S10'!$B$6:$B$13,$A50,'S10'!$E$6:$E$13,"Ambos")+COUNTIFS('Holgura'!$B$6:$B$11,$A50,'Holgura'!$E$6:$E$11,"Diego")+COUNTIFS('Holgura'!$B$6:$B$11,$A50,'Holgura'!$E$6:$E$11,"Ambos")+COUNTIFS('Entrega'!$B$6:$B$9,$A50,'Entrega'!$E$6:$E$9,"Diego")+COUNTIFS('Entrega'!$B$6:$B$9,$A50,'Entrega'!$E$6:$E$9,"Ambos")+COUNTIFS('Defensa'!$B$6:$B$10,$A50,'Defensa'!$E$6:$E$10,"Diego")+COUNTIFS('Defensa'!$B$6:$B$10,$A50,'Defensa'!$E$6:$E$10,"Ambos")</f>
+        <f>COUNTIFS('S1'!$B$6:$B$32,$A50,'S1'!$E$6:$E$32,"Diego")+COUNTIFS('S1'!$B$6:$B$32,$A50,'S1'!$E$6:$E$32,"Ambos")+COUNTIFS('S2'!$B$6:$B$23,$A50,'S2'!$E$6:$E$23,"Diego")+COUNTIFS('S2'!$B$6:$B$23,$A50,'S2'!$E$6:$E$23,"Ambos")+COUNTIFS('S3'!$B$6:$B$24,$A50,'S3'!$E$6:$E$24,"Diego")+COUNTIFS('S3'!$B$6:$B$24,$A50,'S3'!$E$6:$E$24,"Ambos")+COUNTIFS('S4'!$B$6:$B$22,$A50,'S4'!$E$6:$E$22,"Diego")+COUNTIFS('S4'!$B$6:$B$22,$A50,'S4'!$E$6:$E$22,"Ambos")+COUNTIFS('S5'!$B$6:$B$20,$A50,'S5'!$E$6:$E$20,"Diego")+COUNTIFS('S5'!$B$6:$B$20,$A50,'S5'!$E$6:$E$20,"Ambos")+COUNTIFS('S6'!$B$6:$B$17,$A50,'S6'!$E$6:$E$17,"Diego")+COUNTIFS('S6'!$B$6:$B$17,$A50,'S6'!$E$6:$E$17,"Ambos")+COUNTIFS('S7'!$B$6:$B$19,$A50,'S7'!$E$6:$E$19,"Diego")+COUNTIFS('S7'!$B$6:$B$19,$A50,'S7'!$E$6:$E$19,"Ambos")+COUNTIFS('S8'!$B$6:$B$23,$A50,'S8'!$E$6:$E$23,"Diego")+COUNTIFS('S8'!$B$6:$B$23,$A50,'S8'!$E$6:$E$23,"Ambos")+COUNTIFS('S9'!$B$6:$B$15,$A50,'S9'!$E$6:$E$15,"Diego")+COUNTIFS('S9'!$B$6:$B$15,$A50,'S9'!$E$6:$E$15,"Ambos")+COUNTIFS('S10'!$B$6:$B$13,$A50,'S10'!$E$6:$E$13,"Diego")+COUNTIFS('S10'!$B$6:$B$13,$A50,'S10'!$E$6:$E$13,"Ambos")+COUNTIFS('Holgura'!$B$6:$B$11,$A50,'Holgura'!$E$6:$E$11,"Diego")+COUNTIFS('Holgura'!$B$6:$B$11,$A50,'Holgura'!$E$6:$E$11,"Ambos")+COUNTIFS('Entrega'!$B$6:$B$9,$A50,'Entrega'!$E$6:$E$9,"Diego")+COUNTIFS('Entrega'!$B$6:$B$9,$A50,'Entrega'!$E$6:$E$9,"Ambos")+COUNTIFS('Defensa'!$B$6:$B$10,$A50,'Defensa'!$E$6:$E$10,"Diego")+COUNTIFS('Defensa'!$B$6:$B$10,$A50,'Defensa'!$E$6:$E$10,"Ambos")</f>
         <v/>
       </c>
     </row>
@@ -10014,19 +10035,19 @@
         <v/>
       </c>
       <c r="D51" s="21">
-        <f>SUMIFS('S1'!$I$6:$I$32,'S1'!$B$6:$B$32,$A51,'S1'!$E$6:$E$32,"Víctor")+SUMIFS('S1'!$I$6:$I$32,'S1'!$B$6:$B$32,$A51,'S1'!$E$6:$E$32,"Ambos")+SUMIFS('S2'!$I$6:$I$23,'S2'!$B$6:$B$23,$A51,'S2'!$E$6:$E$23,"Víctor")+SUMIFS('S2'!$I$6:$I$23,'S2'!$B$6:$B$23,$A51,'S2'!$E$6:$E$23,"Ambos")+SUMIFS('S3'!$I$6:$I$19,'S3'!$B$6:$B$19,$A51,'S3'!$E$6:$E$19,"Víctor")+SUMIFS('S3'!$I$6:$I$19,'S3'!$B$6:$B$19,$A51,'S3'!$E$6:$E$19,"Ambos")+SUMIFS('S4'!$I$6:$I$20,'S4'!$B$6:$B$20,$A51,'S4'!$E$6:$E$20,"Víctor")+SUMIFS('S4'!$I$6:$I$20,'S4'!$B$6:$B$20,$A51,'S4'!$E$6:$E$20,"Ambos")+SUMIFS('S5'!$I$6:$I$20,'S5'!$B$6:$B$20,$A51,'S5'!$E$6:$E$20,"Víctor")+SUMIFS('S5'!$I$6:$I$20,'S5'!$B$6:$B$20,$A51,'S5'!$E$6:$E$20,"Ambos")+SUMIFS('S6'!$I$6:$I$17,'S6'!$B$6:$B$17,$A51,'S6'!$E$6:$E$17,"Víctor")+SUMIFS('S6'!$I$6:$I$17,'S6'!$B$6:$B$17,$A51,'S6'!$E$6:$E$17,"Ambos")+SUMIFS('S7'!$I$6:$I$19,'S7'!$B$6:$B$19,$A51,'S7'!$E$6:$E$19,"Víctor")+SUMIFS('S7'!$I$6:$I$19,'S7'!$B$6:$B$19,$A51,'S7'!$E$6:$E$19,"Ambos")+SUMIFS('S8'!$I$6:$I$23,'S8'!$B$6:$B$23,$A51,'S8'!$E$6:$E$23,"Víctor")+SUMIFS('S8'!$I$6:$I$23,'S8'!$B$6:$B$23,$A51,'S8'!$E$6:$E$23,"Ambos")+SUMIFS('S9'!$I$6:$I$15,'S9'!$B$6:$B$15,$A51,'S9'!$E$6:$E$15,"Víctor")+SUMIFS('S9'!$I$6:$I$15,'S9'!$B$6:$B$15,$A51,'S9'!$E$6:$E$15,"Ambos")+SUMIFS('S10'!$I$6:$I$13,'S10'!$B$6:$B$13,$A51,'S10'!$E$6:$E$13,"Víctor")+SUMIFS('S10'!$I$6:$I$13,'S10'!$B$6:$B$13,$A51,'S10'!$E$6:$E$13,"Ambos")+SUMIFS('Holgura'!$I$6:$I$11,'Holgura'!$B$6:$B$11,$A51,'Holgura'!$E$6:$E$11,"Víctor")+SUMIFS('Holgura'!$I$6:$I$11,'Holgura'!$B$6:$B$11,$A51,'Holgura'!$E$6:$E$11,"Ambos")+SUMIFS('Entrega'!$I$6:$I$9,'Entrega'!$B$6:$B$9,$A51,'Entrega'!$E$6:$E$9,"Víctor")+SUMIFS('Entrega'!$I$6:$I$9,'Entrega'!$B$6:$B$9,$A51,'Entrega'!$E$6:$E$9,"Ambos")+SUMIFS('Defensa'!$I$6:$I$10,'Defensa'!$B$6:$B$10,$A51,'Defensa'!$E$6:$E$10,"Víctor")+SUMIFS('Defensa'!$I$6:$I$10,'Defensa'!$B$6:$B$10,$A51,'Defensa'!$E$6:$E$10,"Ambos")</f>
+        <f>SUMIFS('S1'!$I$6:$I$32,'S1'!$B$6:$B$32,$A51,'S1'!$E$6:$E$32,"Víctor")+SUMIFS('S1'!$I$6:$I$32,'S1'!$B$6:$B$32,$A51,'S1'!$E$6:$E$32,"Ambos")+SUMIFS('S2'!$I$6:$I$23,'S2'!$B$6:$B$23,$A51,'S2'!$E$6:$E$23,"Víctor")+SUMIFS('S2'!$I$6:$I$23,'S2'!$B$6:$B$23,$A51,'S2'!$E$6:$E$23,"Ambos")+SUMIFS('S3'!$I$6:$I$24,'S3'!$B$6:$B$24,$A51,'S3'!$E$6:$E$24,"Víctor")+SUMIFS('S3'!$I$6:$I$24,'S3'!$B$6:$B$24,$A51,'S3'!$E$6:$E$24,"Ambos")+SUMIFS('S4'!$I$6:$I$22,'S4'!$B$6:$B$22,$A51,'S4'!$E$6:$E$22,"Víctor")+SUMIFS('S4'!$I$6:$I$22,'S4'!$B$6:$B$22,$A51,'S4'!$E$6:$E$22,"Ambos")+SUMIFS('S5'!$I$6:$I$20,'S5'!$B$6:$B$20,$A51,'S5'!$E$6:$E$20,"Víctor")+SUMIFS('S5'!$I$6:$I$20,'S5'!$B$6:$B$20,$A51,'S5'!$E$6:$E$20,"Ambos")+SUMIFS('S6'!$I$6:$I$17,'S6'!$B$6:$B$17,$A51,'S6'!$E$6:$E$17,"Víctor")+SUMIFS('S6'!$I$6:$I$17,'S6'!$B$6:$B$17,$A51,'S6'!$E$6:$E$17,"Ambos")+SUMIFS('S7'!$I$6:$I$19,'S7'!$B$6:$B$19,$A51,'S7'!$E$6:$E$19,"Víctor")+SUMIFS('S7'!$I$6:$I$19,'S7'!$B$6:$B$19,$A51,'S7'!$E$6:$E$19,"Ambos")+SUMIFS('S8'!$I$6:$I$23,'S8'!$B$6:$B$23,$A51,'S8'!$E$6:$E$23,"Víctor")+SUMIFS('S8'!$I$6:$I$23,'S8'!$B$6:$B$23,$A51,'S8'!$E$6:$E$23,"Ambos")+SUMIFS('S9'!$I$6:$I$15,'S9'!$B$6:$B$15,$A51,'S9'!$E$6:$E$15,"Víctor")+SUMIFS('S9'!$I$6:$I$15,'S9'!$B$6:$B$15,$A51,'S9'!$E$6:$E$15,"Ambos")+SUMIFS('S10'!$I$6:$I$13,'S10'!$B$6:$B$13,$A51,'S10'!$E$6:$E$13,"Víctor")+SUMIFS('S10'!$I$6:$I$13,'S10'!$B$6:$B$13,$A51,'S10'!$E$6:$E$13,"Ambos")+SUMIFS('Holgura'!$I$6:$I$11,'Holgura'!$B$6:$B$11,$A51,'Holgura'!$E$6:$E$11,"Víctor")+SUMIFS('Holgura'!$I$6:$I$11,'Holgura'!$B$6:$B$11,$A51,'Holgura'!$E$6:$E$11,"Ambos")+SUMIFS('Entrega'!$I$6:$I$9,'Entrega'!$B$6:$B$9,$A51,'Entrega'!$E$6:$E$9,"Víctor")+SUMIFS('Entrega'!$I$6:$I$9,'Entrega'!$B$6:$B$9,$A51,'Entrega'!$E$6:$E$9,"Ambos")+SUMIFS('Defensa'!$I$6:$I$10,'Defensa'!$B$6:$B$10,$A51,'Defensa'!$E$6:$E$10,"Víctor")+SUMIFS('Defensa'!$I$6:$I$10,'Defensa'!$B$6:$B$10,$A51,'Defensa'!$E$6:$E$10,"Ambos")</f>
         <v/>
       </c>
       <c r="E51" s="21">
-        <f>SUMIFS('S1'!$I$6:$I$32,'S1'!$B$6:$B$32,$A51,'S1'!$E$6:$E$32,"Diego")+SUMIFS('S1'!$I$6:$I$32,'S1'!$B$6:$B$32,$A51,'S1'!$E$6:$E$32,"Ambos")+SUMIFS('S2'!$I$6:$I$23,'S2'!$B$6:$B$23,$A51,'S2'!$E$6:$E$23,"Diego")+SUMIFS('S2'!$I$6:$I$23,'S2'!$B$6:$B$23,$A51,'S2'!$E$6:$E$23,"Ambos")+SUMIFS('S3'!$I$6:$I$19,'S3'!$B$6:$B$19,$A51,'S3'!$E$6:$E$19,"Diego")+SUMIFS('S3'!$I$6:$I$19,'S3'!$B$6:$B$19,$A51,'S3'!$E$6:$E$19,"Ambos")+SUMIFS('S4'!$I$6:$I$20,'S4'!$B$6:$B$20,$A51,'S4'!$E$6:$E$20,"Diego")+SUMIFS('S4'!$I$6:$I$20,'S4'!$B$6:$B$20,$A51,'S4'!$E$6:$E$20,"Ambos")+SUMIFS('S5'!$I$6:$I$20,'S5'!$B$6:$B$20,$A51,'S5'!$E$6:$E$20,"Diego")+SUMIFS('S5'!$I$6:$I$20,'S5'!$B$6:$B$20,$A51,'S5'!$E$6:$E$20,"Ambos")+SUMIFS('S6'!$I$6:$I$17,'S6'!$B$6:$B$17,$A51,'S6'!$E$6:$E$17,"Diego")+SUMIFS('S6'!$I$6:$I$17,'S6'!$B$6:$B$17,$A51,'S6'!$E$6:$E$17,"Ambos")+SUMIFS('S7'!$I$6:$I$19,'S7'!$B$6:$B$19,$A51,'S7'!$E$6:$E$19,"Diego")+SUMIFS('S7'!$I$6:$I$19,'S7'!$B$6:$B$19,$A51,'S7'!$E$6:$E$19,"Ambos")+SUMIFS('S8'!$I$6:$I$23,'S8'!$B$6:$B$23,$A51,'S8'!$E$6:$E$23,"Diego")+SUMIFS('S8'!$I$6:$I$23,'S8'!$B$6:$B$23,$A51,'S8'!$E$6:$E$23,"Ambos")+SUMIFS('S9'!$I$6:$I$15,'S9'!$B$6:$B$15,$A51,'S9'!$E$6:$E$15,"Diego")+SUMIFS('S9'!$I$6:$I$15,'S9'!$B$6:$B$15,$A51,'S9'!$E$6:$E$15,"Ambos")+SUMIFS('S10'!$I$6:$I$13,'S10'!$B$6:$B$13,$A51,'S10'!$E$6:$E$13,"Diego")+SUMIFS('S10'!$I$6:$I$13,'S10'!$B$6:$B$13,$A51,'S10'!$E$6:$E$13,"Ambos")+SUMIFS('Holgura'!$I$6:$I$11,'Holgura'!$B$6:$B$11,$A51,'Holgura'!$E$6:$E$11,"Diego")+SUMIFS('Holgura'!$I$6:$I$11,'Holgura'!$B$6:$B$11,$A51,'Holgura'!$E$6:$E$11,"Ambos")+SUMIFS('Entrega'!$I$6:$I$9,'Entrega'!$B$6:$B$9,$A51,'Entrega'!$E$6:$E$9,"Diego")+SUMIFS('Entrega'!$I$6:$I$9,'Entrega'!$B$6:$B$9,$A51,'Entrega'!$E$6:$E$9,"Ambos")+SUMIFS('Defensa'!$I$6:$I$10,'Defensa'!$B$6:$B$10,$A51,'Defensa'!$E$6:$E$10,"Diego")+SUMIFS('Defensa'!$I$6:$I$10,'Defensa'!$B$6:$B$10,$A51,'Defensa'!$E$6:$E$10,"Ambos")</f>
+        <f>SUMIFS('S1'!$I$6:$I$32,'S1'!$B$6:$B$32,$A51,'S1'!$E$6:$E$32,"Diego")+SUMIFS('S1'!$I$6:$I$32,'S1'!$B$6:$B$32,$A51,'S1'!$E$6:$E$32,"Ambos")+SUMIFS('S2'!$I$6:$I$23,'S2'!$B$6:$B$23,$A51,'S2'!$E$6:$E$23,"Diego")+SUMIFS('S2'!$I$6:$I$23,'S2'!$B$6:$B$23,$A51,'S2'!$E$6:$E$23,"Ambos")+SUMIFS('S3'!$I$6:$I$24,'S3'!$B$6:$B$24,$A51,'S3'!$E$6:$E$24,"Diego")+SUMIFS('S3'!$I$6:$I$24,'S3'!$B$6:$B$24,$A51,'S3'!$E$6:$E$24,"Ambos")+SUMIFS('S4'!$I$6:$I$22,'S4'!$B$6:$B$22,$A51,'S4'!$E$6:$E$22,"Diego")+SUMIFS('S4'!$I$6:$I$22,'S4'!$B$6:$B$22,$A51,'S4'!$E$6:$E$22,"Ambos")+SUMIFS('S5'!$I$6:$I$20,'S5'!$B$6:$B$20,$A51,'S5'!$E$6:$E$20,"Diego")+SUMIFS('S5'!$I$6:$I$20,'S5'!$B$6:$B$20,$A51,'S5'!$E$6:$E$20,"Ambos")+SUMIFS('S6'!$I$6:$I$17,'S6'!$B$6:$B$17,$A51,'S6'!$E$6:$E$17,"Diego")+SUMIFS('S6'!$I$6:$I$17,'S6'!$B$6:$B$17,$A51,'S6'!$E$6:$E$17,"Ambos")+SUMIFS('S7'!$I$6:$I$19,'S7'!$B$6:$B$19,$A51,'S7'!$E$6:$E$19,"Diego")+SUMIFS('S7'!$I$6:$I$19,'S7'!$B$6:$B$19,$A51,'S7'!$E$6:$E$19,"Ambos")+SUMIFS('S8'!$I$6:$I$23,'S8'!$B$6:$B$23,$A51,'S8'!$E$6:$E$23,"Diego")+SUMIFS('S8'!$I$6:$I$23,'S8'!$B$6:$B$23,$A51,'S8'!$E$6:$E$23,"Ambos")+SUMIFS('S9'!$I$6:$I$15,'S9'!$B$6:$B$15,$A51,'S9'!$E$6:$E$15,"Diego")+SUMIFS('S9'!$I$6:$I$15,'S9'!$B$6:$B$15,$A51,'S9'!$E$6:$E$15,"Ambos")+SUMIFS('S10'!$I$6:$I$13,'S10'!$B$6:$B$13,$A51,'S10'!$E$6:$E$13,"Diego")+SUMIFS('S10'!$I$6:$I$13,'S10'!$B$6:$B$13,$A51,'S10'!$E$6:$E$13,"Ambos")+SUMIFS('Holgura'!$I$6:$I$11,'Holgura'!$B$6:$B$11,$A51,'Holgura'!$E$6:$E$11,"Diego")+SUMIFS('Holgura'!$I$6:$I$11,'Holgura'!$B$6:$B$11,$A51,'Holgura'!$E$6:$E$11,"Ambos")+SUMIFS('Entrega'!$I$6:$I$9,'Entrega'!$B$6:$B$9,$A51,'Entrega'!$E$6:$E$9,"Diego")+SUMIFS('Entrega'!$I$6:$I$9,'Entrega'!$B$6:$B$9,$A51,'Entrega'!$E$6:$E$9,"Ambos")+SUMIFS('Defensa'!$I$6:$I$10,'Defensa'!$B$6:$B$10,$A51,'Defensa'!$E$6:$E$10,"Diego")+SUMIFS('Defensa'!$I$6:$I$10,'Defensa'!$B$6:$B$10,$A51,'Defensa'!$E$6:$E$10,"Ambos")</f>
         <v/>
       </c>
       <c r="F51" s="21">
-        <f>COUNTIFS('S1'!$B$6:$B$32,$A51,'S1'!$E$6:$E$32,"Víctor")+COUNTIFS('S1'!$B$6:$B$32,$A51,'S1'!$E$6:$E$32,"Ambos")+COUNTIFS('S2'!$B$6:$B$23,$A51,'S2'!$E$6:$E$23,"Víctor")+COUNTIFS('S2'!$B$6:$B$23,$A51,'S2'!$E$6:$E$23,"Ambos")+COUNTIFS('S3'!$B$6:$B$19,$A51,'S3'!$E$6:$E$19,"Víctor")+COUNTIFS('S3'!$B$6:$B$19,$A51,'S3'!$E$6:$E$19,"Ambos")+COUNTIFS('S4'!$B$6:$B$20,$A51,'S4'!$E$6:$E$20,"Víctor")+COUNTIFS('S4'!$B$6:$B$20,$A51,'S4'!$E$6:$E$20,"Ambos")+COUNTIFS('S5'!$B$6:$B$20,$A51,'S5'!$E$6:$E$20,"Víctor")+COUNTIFS('S5'!$B$6:$B$20,$A51,'S5'!$E$6:$E$20,"Ambos")+COUNTIFS('S6'!$B$6:$B$17,$A51,'S6'!$E$6:$E$17,"Víctor")+COUNTIFS('S6'!$B$6:$B$17,$A51,'S6'!$E$6:$E$17,"Ambos")+COUNTIFS('S7'!$B$6:$B$19,$A51,'S7'!$E$6:$E$19,"Víctor")+COUNTIFS('S7'!$B$6:$B$19,$A51,'S7'!$E$6:$E$19,"Ambos")+COUNTIFS('S8'!$B$6:$B$23,$A51,'S8'!$E$6:$E$23,"Víctor")+COUNTIFS('S8'!$B$6:$B$23,$A51,'S8'!$E$6:$E$23,"Ambos")+COUNTIFS('S9'!$B$6:$B$15,$A51,'S9'!$E$6:$E$15,"Víctor")+COUNTIFS('S9'!$B$6:$B$15,$A51,'S9'!$E$6:$E$15,"Ambos")+COUNTIFS('S10'!$B$6:$B$13,$A51,'S10'!$E$6:$E$13,"Víctor")+COUNTIFS('S10'!$B$6:$B$13,$A51,'S10'!$E$6:$E$13,"Ambos")+COUNTIFS('Holgura'!$B$6:$B$11,$A51,'Holgura'!$E$6:$E$11,"Víctor")+COUNTIFS('Holgura'!$B$6:$B$11,$A51,'Holgura'!$E$6:$E$11,"Ambos")+COUNTIFS('Entrega'!$B$6:$B$9,$A51,'Entrega'!$E$6:$E$9,"Víctor")+COUNTIFS('Entrega'!$B$6:$B$9,$A51,'Entrega'!$E$6:$E$9,"Ambos")+COUNTIFS('Defensa'!$B$6:$B$10,$A51,'Defensa'!$E$6:$E$10,"Víctor")+COUNTIFS('Defensa'!$B$6:$B$10,$A51,'Defensa'!$E$6:$E$10,"Ambos")</f>
+        <f>COUNTIFS('S1'!$B$6:$B$32,$A51,'S1'!$E$6:$E$32,"Víctor")+COUNTIFS('S1'!$B$6:$B$32,$A51,'S1'!$E$6:$E$32,"Ambos")+COUNTIFS('S2'!$B$6:$B$23,$A51,'S2'!$E$6:$E$23,"Víctor")+COUNTIFS('S2'!$B$6:$B$23,$A51,'S2'!$E$6:$E$23,"Ambos")+COUNTIFS('S3'!$B$6:$B$24,$A51,'S3'!$E$6:$E$24,"Víctor")+COUNTIFS('S3'!$B$6:$B$24,$A51,'S3'!$E$6:$E$24,"Ambos")+COUNTIFS('S4'!$B$6:$B$22,$A51,'S4'!$E$6:$E$22,"Víctor")+COUNTIFS('S4'!$B$6:$B$22,$A51,'S4'!$E$6:$E$22,"Ambos")+COUNTIFS('S5'!$B$6:$B$20,$A51,'S5'!$E$6:$E$20,"Víctor")+COUNTIFS('S5'!$B$6:$B$20,$A51,'S5'!$E$6:$E$20,"Ambos")+COUNTIFS('S6'!$B$6:$B$17,$A51,'S6'!$E$6:$E$17,"Víctor")+COUNTIFS('S6'!$B$6:$B$17,$A51,'S6'!$E$6:$E$17,"Ambos")+COUNTIFS('S7'!$B$6:$B$19,$A51,'S7'!$E$6:$E$19,"Víctor")+COUNTIFS('S7'!$B$6:$B$19,$A51,'S7'!$E$6:$E$19,"Ambos")+COUNTIFS('S8'!$B$6:$B$23,$A51,'S8'!$E$6:$E$23,"Víctor")+COUNTIFS('S8'!$B$6:$B$23,$A51,'S8'!$E$6:$E$23,"Ambos")+COUNTIFS('S9'!$B$6:$B$15,$A51,'S9'!$E$6:$E$15,"Víctor")+COUNTIFS('S9'!$B$6:$B$15,$A51,'S9'!$E$6:$E$15,"Ambos")+COUNTIFS('S10'!$B$6:$B$13,$A51,'S10'!$E$6:$E$13,"Víctor")+COUNTIFS('S10'!$B$6:$B$13,$A51,'S10'!$E$6:$E$13,"Ambos")+COUNTIFS('Holgura'!$B$6:$B$11,$A51,'Holgura'!$E$6:$E$11,"Víctor")+COUNTIFS('Holgura'!$B$6:$B$11,$A51,'Holgura'!$E$6:$E$11,"Ambos")+COUNTIFS('Entrega'!$B$6:$B$9,$A51,'Entrega'!$E$6:$E$9,"Víctor")+COUNTIFS('Entrega'!$B$6:$B$9,$A51,'Entrega'!$E$6:$E$9,"Ambos")+COUNTIFS('Defensa'!$B$6:$B$10,$A51,'Defensa'!$E$6:$E$10,"Víctor")+COUNTIFS('Defensa'!$B$6:$B$10,$A51,'Defensa'!$E$6:$E$10,"Ambos")</f>
         <v/>
       </c>
       <c r="G51" s="21">
-        <f>COUNTIFS('S1'!$B$6:$B$32,$A51,'S1'!$E$6:$E$32,"Diego")+COUNTIFS('S1'!$B$6:$B$32,$A51,'S1'!$E$6:$E$32,"Ambos")+COUNTIFS('S2'!$B$6:$B$23,$A51,'S2'!$E$6:$E$23,"Diego")+COUNTIFS('S2'!$B$6:$B$23,$A51,'S2'!$E$6:$E$23,"Ambos")+COUNTIFS('S3'!$B$6:$B$19,$A51,'S3'!$E$6:$E$19,"Diego")+COUNTIFS('S3'!$B$6:$B$19,$A51,'S3'!$E$6:$E$19,"Ambos")+COUNTIFS('S4'!$B$6:$B$20,$A51,'S4'!$E$6:$E$20,"Diego")+COUNTIFS('S4'!$B$6:$B$20,$A51,'S4'!$E$6:$E$20,"Ambos")+COUNTIFS('S5'!$B$6:$B$20,$A51,'S5'!$E$6:$E$20,"Diego")+COUNTIFS('S5'!$B$6:$B$20,$A51,'S5'!$E$6:$E$20,"Ambos")+COUNTIFS('S6'!$B$6:$B$17,$A51,'S6'!$E$6:$E$17,"Diego")+COUNTIFS('S6'!$B$6:$B$17,$A51,'S6'!$E$6:$E$17,"Ambos")+COUNTIFS('S7'!$B$6:$B$19,$A51,'S7'!$E$6:$E$19,"Diego")+COUNTIFS('S7'!$B$6:$B$19,$A51,'S7'!$E$6:$E$19,"Ambos")+COUNTIFS('S8'!$B$6:$B$23,$A51,'S8'!$E$6:$E$23,"Diego")+COUNTIFS('S8'!$B$6:$B$23,$A51,'S8'!$E$6:$E$23,"Ambos")+COUNTIFS('S9'!$B$6:$B$15,$A51,'S9'!$E$6:$E$15,"Diego")+COUNTIFS('S9'!$B$6:$B$15,$A51,'S9'!$E$6:$E$15,"Ambos")+COUNTIFS('S10'!$B$6:$B$13,$A51,'S10'!$E$6:$E$13,"Diego")+COUNTIFS('S10'!$B$6:$B$13,$A51,'S10'!$E$6:$E$13,"Ambos")+COUNTIFS('Holgura'!$B$6:$B$11,$A51,'Holgura'!$E$6:$E$11,"Diego")+COUNTIFS('Holgura'!$B$6:$B$11,$A51,'Holgura'!$E$6:$E$11,"Ambos")+COUNTIFS('Entrega'!$B$6:$B$9,$A51,'Entrega'!$E$6:$E$9,"Diego")+COUNTIFS('Entrega'!$B$6:$B$9,$A51,'Entrega'!$E$6:$E$9,"Ambos")+COUNTIFS('Defensa'!$B$6:$B$10,$A51,'Defensa'!$E$6:$E$10,"Diego")+COUNTIFS('Defensa'!$B$6:$B$10,$A51,'Defensa'!$E$6:$E$10,"Ambos")</f>
+        <f>COUNTIFS('S1'!$B$6:$B$32,$A51,'S1'!$E$6:$E$32,"Diego")+COUNTIFS('S1'!$B$6:$B$32,$A51,'S1'!$E$6:$E$32,"Ambos")+COUNTIFS('S2'!$B$6:$B$23,$A51,'S2'!$E$6:$E$23,"Diego")+COUNTIFS('S2'!$B$6:$B$23,$A51,'S2'!$E$6:$E$23,"Ambos")+COUNTIFS('S3'!$B$6:$B$24,$A51,'S3'!$E$6:$E$24,"Diego")+COUNTIFS('S3'!$B$6:$B$24,$A51,'S3'!$E$6:$E$24,"Ambos")+COUNTIFS('S4'!$B$6:$B$22,$A51,'S4'!$E$6:$E$22,"Diego")+COUNTIFS('S4'!$B$6:$B$22,$A51,'S4'!$E$6:$E$22,"Ambos")+COUNTIFS('S5'!$B$6:$B$20,$A51,'S5'!$E$6:$E$20,"Diego")+COUNTIFS('S5'!$B$6:$B$20,$A51,'S5'!$E$6:$E$20,"Ambos")+COUNTIFS('S6'!$B$6:$B$17,$A51,'S6'!$E$6:$E$17,"Diego")+COUNTIFS('S6'!$B$6:$B$17,$A51,'S6'!$E$6:$E$17,"Ambos")+COUNTIFS('S7'!$B$6:$B$19,$A51,'S7'!$E$6:$E$19,"Diego")+COUNTIFS('S7'!$B$6:$B$19,$A51,'S7'!$E$6:$E$19,"Ambos")+COUNTIFS('S8'!$B$6:$B$23,$A51,'S8'!$E$6:$E$23,"Diego")+COUNTIFS('S8'!$B$6:$B$23,$A51,'S8'!$E$6:$E$23,"Ambos")+COUNTIFS('S9'!$B$6:$B$15,$A51,'S9'!$E$6:$E$15,"Diego")+COUNTIFS('S9'!$B$6:$B$15,$A51,'S9'!$E$6:$E$15,"Ambos")+COUNTIFS('S10'!$B$6:$B$13,$A51,'S10'!$E$6:$E$13,"Diego")+COUNTIFS('S10'!$B$6:$B$13,$A51,'S10'!$E$6:$E$13,"Ambos")+COUNTIFS('Holgura'!$B$6:$B$11,$A51,'Holgura'!$E$6:$E$11,"Diego")+COUNTIFS('Holgura'!$B$6:$B$11,$A51,'Holgura'!$E$6:$E$11,"Ambos")+COUNTIFS('Entrega'!$B$6:$B$9,$A51,'Entrega'!$E$6:$E$9,"Diego")+COUNTIFS('Entrega'!$B$6:$B$9,$A51,'Entrega'!$E$6:$E$9,"Ambos")+COUNTIFS('Defensa'!$B$6:$B$10,$A51,'Defensa'!$E$6:$E$10,"Diego")+COUNTIFS('Defensa'!$B$6:$B$10,$A51,'Defensa'!$E$6:$E$10,"Ambos")</f>
         <v/>
       </c>
     </row>
@@ -10043,19 +10064,19 @@
         <v/>
       </c>
       <c r="D52" s="21">
-        <f>SUMIFS('S1'!$I$6:$I$32,'S1'!$B$6:$B$32,$A52,'S1'!$E$6:$E$32,"Víctor")+SUMIFS('S1'!$I$6:$I$32,'S1'!$B$6:$B$32,$A52,'S1'!$E$6:$E$32,"Ambos")+SUMIFS('S2'!$I$6:$I$23,'S2'!$B$6:$B$23,$A52,'S2'!$E$6:$E$23,"Víctor")+SUMIFS('S2'!$I$6:$I$23,'S2'!$B$6:$B$23,$A52,'S2'!$E$6:$E$23,"Ambos")+SUMIFS('S3'!$I$6:$I$19,'S3'!$B$6:$B$19,$A52,'S3'!$E$6:$E$19,"Víctor")+SUMIFS('S3'!$I$6:$I$19,'S3'!$B$6:$B$19,$A52,'S3'!$E$6:$E$19,"Ambos")+SUMIFS('S4'!$I$6:$I$20,'S4'!$B$6:$B$20,$A52,'S4'!$E$6:$E$20,"Víctor")+SUMIFS('S4'!$I$6:$I$20,'S4'!$B$6:$B$20,$A52,'S4'!$E$6:$E$20,"Ambos")+SUMIFS('S5'!$I$6:$I$20,'S5'!$B$6:$B$20,$A52,'S5'!$E$6:$E$20,"Víctor")+SUMIFS('S5'!$I$6:$I$20,'S5'!$B$6:$B$20,$A52,'S5'!$E$6:$E$20,"Ambos")+SUMIFS('S6'!$I$6:$I$17,'S6'!$B$6:$B$17,$A52,'S6'!$E$6:$E$17,"Víctor")+SUMIFS('S6'!$I$6:$I$17,'S6'!$B$6:$B$17,$A52,'S6'!$E$6:$E$17,"Ambos")+SUMIFS('S7'!$I$6:$I$19,'S7'!$B$6:$B$19,$A52,'S7'!$E$6:$E$19,"Víctor")+SUMIFS('S7'!$I$6:$I$19,'S7'!$B$6:$B$19,$A52,'S7'!$E$6:$E$19,"Ambos")+SUMIFS('S8'!$I$6:$I$23,'S8'!$B$6:$B$23,$A52,'S8'!$E$6:$E$23,"Víctor")+SUMIFS('S8'!$I$6:$I$23,'S8'!$B$6:$B$23,$A52,'S8'!$E$6:$E$23,"Ambos")+SUMIFS('S9'!$I$6:$I$15,'S9'!$B$6:$B$15,$A52,'S9'!$E$6:$E$15,"Víctor")+SUMIFS('S9'!$I$6:$I$15,'S9'!$B$6:$B$15,$A52,'S9'!$E$6:$E$15,"Ambos")+SUMIFS('S10'!$I$6:$I$13,'S10'!$B$6:$B$13,$A52,'S10'!$E$6:$E$13,"Víctor")+SUMIFS('S10'!$I$6:$I$13,'S10'!$B$6:$B$13,$A52,'S10'!$E$6:$E$13,"Ambos")+SUMIFS('Holgura'!$I$6:$I$11,'Holgura'!$B$6:$B$11,$A52,'Holgura'!$E$6:$E$11,"Víctor")+SUMIFS('Holgura'!$I$6:$I$11,'Holgura'!$B$6:$B$11,$A52,'Holgura'!$E$6:$E$11,"Ambos")+SUMIFS('Entrega'!$I$6:$I$9,'Entrega'!$B$6:$B$9,$A52,'Entrega'!$E$6:$E$9,"Víctor")+SUMIFS('Entrega'!$I$6:$I$9,'Entrega'!$B$6:$B$9,$A52,'Entrega'!$E$6:$E$9,"Ambos")+SUMIFS('Defensa'!$I$6:$I$10,'Defensa'!$B$6:$B$10,$A52,'Defensa'!$E$6:$E$10,"Víctor")+SUMIFS('Defensa'!$I$6:$I$10,'Defensa'!$B$6:$B$10,$A52,'Defensa'!$E$6:$E$10,"Ambos")</f>
+        <f>SUMIFS('S1'!$I$6:$I$32,'S1'!$B$6:$B$32,$A52,'S1'!$E$6:$E$32,"Víctor")+SUMIFS('S1'!$I$6:$I$32,'S1'!$B$6:$B$32,$A52,'S1'!$E$6:$E$32,"Ambos")+SUMIFS('S2'!$I$6:$I$23,'S2'!$B$6:$B$23,$A52,'S2'!$E$6:$E$23,"Víctor")+SUMIFS('S2'!$I$6:$I$23,'S2'!$B$6:$B$23,$A52,'S2'!$E$6:$E$23,"Ambos")+SUMIFS('S3'!$I$6:$I$24,'S3'!$B$6:$B$24,$A52,'S3'!$E$6:$E$24,"Víctor")+SUMIFS('S3'!$I$6:$I$24,'S3'!$B$6:$B$24,$A52,'S3'!$E$6:$E$24,"Ambos")+SUMIFS('S4'!$I$6:$I$22,'S4'!$B$6:$B$22,$A52,'S4'!$E$6:$E$22,"Víctor")+SUMIFS('S4'!$I$6:$I$22,'S4'!$B$6:$B$22,$A52,'S4'!$E$6:$E$22,"Ambos")+SUMIFS('S5'!$I$6:$I$20,'S5'!$B$6:$B$20,$A52,'S5'!$E$6:$E$20,"Víctor")+SUMIFS('S5'!$I$6:$I$20,'S5'!$B$6:$B$20,$A52,'S5'!$E$6:$E$20,"Ambos")+SUMIFS('S6'!$I$6:$I$17,'S6'!$B$6:$B$17,$A52,'S6'!$E$6:$E$17,"Víctor")+SUMIFS('S6'!$I$6:$I$17,'S6'!$B$6:$B$17,$A52,'S6'!$E$6:$E$17,"Ambos")+SUMIFS('S7'!$I$6:$I$19,'S7'!$B$6:$B$19,$A52,'S7'!$E$6:$E$19,"Víctor")+SUMIFS('S7'!$I$6:$I$19,'S7'!$B$6:$B$19,$A52,'S7'!$E$6:$E$19,"Ambos")+SUMIFS('S8'!$I$6:$I$23,'S8'!$B$6:$B$23,$A52,'S8'!$E$6:$E$23,"Víctor")+SUMIFS('S8'!$I$6:$I$23,'S8'!$B$6:$B$23,$A52,'S8'!$E$6:$E$23,"Ambos")+SUMIFS('S9'!$I$6:$I$15,'S9'!$B$6:$B$15,$A52,'S9'!$E$6:$E$15,"Víctor")+SUMIFS('S9'!$I$6:$I$15,'S9'!$B$6:$B$15,$A52,'S9'!$E$6:$E$15,"Ambos")+SUMIFS('S10'!$I$6:$I$13,'S10'!$B$6:$B$13,$A52,'S10'!$E$6:$E$13,"Víctor")+SUMIFS('S10'!$I$6:$I$13,'S10'!$B$6:$B$13,$A52,'S10'!$E$6:$E$13,"Ambos")+SUMIFS('Holgura'!$I$6:$I$11,'Holgura'!$B$6:$B$11,$A52,'Holgura'!$E$6:$E$11,"Víctor")+SUMIFS('Holgura'!$I$6:$I$11,'Holgura'!$B$6:$B$11,$A52,'Holgura'!$E$6:$E$11,"Ambos")+SUMIFS('Entrega'!$I$6:$I$9,'Entrega'!$B$6:$B$9,$A52,'Entrega'!$E$6:$E$9,"Víctor")+SUMIFS('Entrega'!$I$6:$I$9,'Entrega'!$B$6:$B$9,$A52,'Entrega'!$E$6:$E$9,"Ambos")+SUMIFS('Defensa'!$I$6:$I$10,'Defensa'!$B$6:$B$10,$A52,'Defensa'!$E$6:$E$10,"Víctor")+SUMIFS('Defensa'!$I$6:$I$10,'Defensa'!$B$6:$B$10,$A52,'Defensa'!$E$6:$E$10,"Ambos")</f>
         <v/>
       </c>
       <c r="E52" s="21">
-        <f>SUMIFS('S1'!$I$6:$I$32,'S1'!$B$6:$B$32,$A52,'S1'!$E$6:$E$32,"Diego")+SUMIFS('S1'!$I$6:$I$32,'S1'!$B$6:$B$32,$A52,'S1'!$E$6:$E$32,"Ambos")+SUMIFS('S2'!$I$6:$I$23,'S2'!$B$6:$B$23,$A52,'S2'!$E$6:$E$23,"Diego")+SUMIFS('S2'!$I$6:$I$23,'S2'!$B$6:$B$23,$A52,'S2'!$E$6:$E$23,"Ambos")+SUMIFS('S3'!$I$6:$I$19,'S3'!$B$6:$B$19,$A52,'S3'!$E$6:$E$19,"Diego")+SUMIFS('S3'!$I$6:$I$19,'S3'!$B$6:$B$19,$A52,'S3'!$E$6:$E$19,"Ambos")+SUMIFS('S4'!$I$6:$I$20,'S4'!$B$6:$B$20,$A52,'S4'!$E$6:$E$20,"Diego")+SUMIFS('S4'!$I$6:$I$20,'S4'!$B$6:$B$20,$A52,'S4'!$E$6:$E$20,"Ambos")+SUMIFS('S5'!$I$6:$I$20,'S5'!$B$6:$B$20,$A52,'S5'!$E$6:$E$20,"Diego")+SUMIFS('S5'!$I$6:$I$20,'S5'!$B$6:$B$20,$A52,'S5'!$E$6:$E$20,"Ambos")+SUMIFS('S6'!$I$6:$I$17,'S6'!$B$6:$B$17,$A52,'S6'!$E$6:$E$17,"Diego")+SUMIFS('S6'!$I$6:$I$17,'S6'!$B$6:$B$17,$A52,'S6'!$E$6:$E$17,"Ambos")+SUMIFS('S7'!$I$6:$I$19,'S7'!$B$6:$B$19,$A52,'S7'!$E$6:$E$19,"Diego")+SUMIFS('S7'!$I$6:$I$19,'S7'!$B$6:$B$19,$A52,'S7'!$E$6:$E$19,"Ambos")+SUMIFS('S8'!$I$6:$I$23,'S8'!$B$6:$B$23,$A52,'S8'!$E$6:$E$23,"Diego")+SUMIFS('S8'!$I$6:$I$23,'S8'!$B$6:$B$23,$A52,'S8'!$E$6:$E$23,"Ambos")+SUMIFS('S9'!$I$6:$I$15,'S9'!$B$6:$B$15,$A52,'S9'!$E$6:$E$15,"Diego")+SUMIFS('S9'!$I$6:$I$15,'S9'!$B$6:$B$15,$A52,'S9'!$E$6:$E$15,"Ambos")+SUMIFS('S10'!$I$6:$I$13,'S10'!$B$6:$B$13,$A52,'S10'!$E$6:$E$13,"Diego")+SUMIFS('S10'!$I$6:$I$13,'S10'!$B$6:$B$13,$A52,'S10'!$E$6:$E$13,"Ambos")+SUMIFS('Holgura'!$I$6:$I$11,'Holgura'!$B$6:$B$11,$A52,'Holgura'!$E$6:$E$11,"Diego")+SUMIFS('Holgura'!$I$6:$I$11,'Holgura'!$B$6:$B$11,$A52,'Holgura'!$E$6:$E$11,"Ambos")+SUMIFS('Entrega'!$I$6:$I$9,'Entrega'!$B$6:$B$9,$A52,'Entrega'!$E$6:$E$9,"Diego")+SUMIFS('Entrega'!$I$6:$I$9,'Entrega'!$B$6:$B$9,$A52,'Entrega'!$E$6:$E$9,"Ambos")+SUMIFS('Defensa'!$I$6:$I$10,'Defensa'!$B$6:$B$10,$A52,'Defensa'!$E$6:$E$10,"Diego")+SUMIFS('Defensa'!$I$6:$I$10,'Defensa'!$B$6:$B$10,$A52,'Defensa'!$E$6:$E$10,"Ambos")</f>
+        <f>SUMIFS('S1'!$I$6:$I$32,'S1'!$B$6:$B$32,$A52,'S1'!$E$6:$E$32,"Diego")+SUMIFS('S1'!$I$6:$I$32,'S1'!$B$6:$B$32,$A52,'S1'!$E$6:$E$32,"Ambos")+SUMIFS('S2'!$I$6:$I$23,'S2'!$B$6:$B$23,$A52,'S2'!$E$6:$E$23,"Diego")+SUMIFS('S2'!$I$6:$I$23,'S2'!$B$6:$B$23,$A52,'S2'!$E$6:$E$23,"Ambos")+SUMIFS('S3'!$I$6:$I$24,'S3'!$B$6:$B$24,$A52,'S3'!$E$6:$E$24,"Diego")+SUMIFS('S3'!$I$6:$I$24,'S3'!$B$6:$B$24,$A52,'S3'!$E$6:$E$24,"Ambos")+SUMIFS('S4'!$I$6:$I$22,'S4'!$B$6:$B$22,$A52,'S4'!$E$6:$E$22,"Diego")+SUMIFS('S4'!$I$6:$I$22,'S4'!$B$6:$B$22,$A52,'S4'!$E$6:$E$22,"Ambos")+SUMIFS('S5'!$I$6:$I$20,'S5'!$B$6:$B$20,$A52,'S5'!$E$6:$E$20,"Diego")+SUMIFS('S5'!$I$6:$I$20,'S5'!$B$6:$B$20,$A52,'S5'!$E$6:$E$20,"Ambos")+SUMIFS('S6'!$I$6:$I$17,'S6'!$B$6:$B$17,$A52,'S6'!$E$6:$E$17,"Diego")+SUMIFS('S6'!$I$6:$I$17,'S6'!$B$6:$B$17,$A52,'S6'!$E$6:$E$17,"Ambos")+SUMIFS('S7'!$I$6:$I$19,'S7'!$B$6:$B$19,$A52,'S7'!$E$6:$E$19,"Diego")+SUMIFS('S7'!$I$6:$I$19,'S7'!$B$6:$B$19,$A52,'S7'!$E$6:$E$19,"Ambos")+SUMIFS('S8'!$I$6:$I$23,'S8'!$B$6:$B$23,$A52,'S8'!$E$6:$E$23,"Diego")+SUMIFS('S8'!$I$6:$I$23,'S8'!$B$6:$B$23,$A52,'S8'!$E$6:$E$23,"Ambos")+SUMIFS('S9'!$I$6:$I$15,'S9'!$B$6:$B$15,$A52,'S9'!$E$6:$E$15,"Diego")+SUMIFS('S9'!$I$6:$I$15,'S9'!$B$6:$B$15,$A52,'S9'!$E$6:$E$15,"Ambos")+SUMIFS('S10'!$I$6:$I$13,'S10'!$B$6:$B$13,$A52,'S10'!$E$6:$E$13,"Diego")+SUMIFS('S10'!$I$6:$I$13,'S10'!$B$6:$B$13,$A52,'S10'!$E$6:$E$13,"Ambos")+SUMIFS('Holgura'!$I$6:$I$11,'Holgura'!$B$6:$B$11,$A52,'Holgura'!$E$6:$E$11,"Diego")+SUMIFS('Holgura'!$I$6:$I$11,'Holgura'!$B$6:$B$11,$A52,'Holgura'!$E$6:$E$11,"Ambos")+SUMIFS('Entrega'!$I$6:$I$9,'Entrega'!$B$6:$B$9,$A52,'Entrega'!$E$6:$E$9,"Diego")+SUMIFS('Entrega'!$I$6:$I$9,'Entrega'!$B$6:$B$9,$A52,'Entrega'!$E$6:$E$9,"Ambos")+SUMIFS('Defensa'!$I$6:$I$10,'Defensa'!$B$6:$B$10,$A52,'Defensa'!$E$6:$E$10,"Diego")+SUMIFS('Defensa'!$I$6:$I$10,'Defensa'!$B$6:$B$10,$A52,'Defensa'!$E$6:$E$10,"Ambos")</f>
         <v/>
       </c>
       <c r="F52" s="21">
-        <f>COUNTIFS('S1'!$B$6:$B$32,$A52,'S1'!$E$6:$E$32,"Víctor")+COUNTIFS('S1'!$B$6:$B$32,$A52,'S1'!$E$6:$E$32,"Ambos")+COUNTIFS('S2'!$B$6:$B$23,$A52,'S2'!$E$6:$E$23,"Víctor")+COUNTIFS('S2'!$B$6:$B$23,$A52,'S2'!$E$6:$E$23,"Ambos")+COUNTIFS('S3'!$B$6:$B$19,$A52,'S3'!$E$6:$E$19,"Víctor")+COUNTIFS('S3'!$B$6:$B$19,$A52,'S3'!$E$6:$E$19,"Ambos")+COUNTIFS('S4'!$B$6:$B$20,$A52,'S4'!$E$6:$E$20,"Víctor")+COUNTIFS('S4'!$B$6:$B$20,$A52,'S4'!$E$6:$E$20,"Ambos")+COUNTIFS('S5'!$B$6:$B$20,$A52,'S5'!$E$6:$E$20,"Víctor")+COUNTIFS('S5'!$B$6:$B$20,$A52,'S5'!$E$6:$E$20,"Ambos")+COUNTIFS('S6'!$B$6:$B$17,$A52,'S6'!$E$6:$E$17,"Víctor")+COUNTIFS('S6'!$B$6:$B$17,$A52,'S6'!$E$6:$E$17,"Ambos")+COUNTIFS('S7'!$B$6:$B$19,$A52,'S7'!$E$6:$E$19,"Víctor")+COUNTIFS('S7'!$B$6:$B$19,$A52,'S7'!$E$6:$E$19,"Ambos")+COUNTIFS('S8'!$B$6:$B$23,$A52,'S8'!$E$6:$E$23,"Víctor")+COUNTIFS('S8'!$B$6:$B$23,$A52,'S8'!$E$6:$E$23,"Ambos")+COUNTIFS('S9'!$B$6:$B$15,$A52,'S9'!$E$6:$E$15,"Víctor")+COUNTIFS('S9'!$B$6:$B$15,$A52,'S9'!$E$6:$E$15,"Ambos")+COUNTIFS('S10'!$B$6:$B$13,$A52,'S10'!$E$6:$E$13,"Víctor")+COUNTIFS('S10'!$B$6:$B$13,$A52,'S10'!$E$6:$E$13,"Ambos")+COUNTIFS('Holgura'!$B$6:$B$11,$A52,'Holgura'!$E$6:$E$11,"Víctor")+COUNTIFS('Holgura'!$B$6:$B$11,$A52,'Holgura'!$E$6:$E$11,"Ambos")+COUNTIFS('Entrega'!$B$6:$B$9,$A52,'Entrega'!$E$6:$E$9,"Víctor")+COUNTIFS('Entrega'!$B$6:$B$9,$A52,'Entrega'!$E$6:$E$9,"Ambos")+COUNTIFS('Defensa'!$B$6:$B$10,$A52,'Defensa'!$E$6:$E$10,"Víctor")+COUNTIFS('Defensa'!$B$6:$B$10,$A52,'Defensa'!$E$6:$E$10,"Ambos")</f>
+        <f>COUNTIFS('S1'!$B$6:$B$32,$A52,'S1'!$E$6:$E$32,"Víctor")+COUNTIFS('S1'!$B$6:$B$32,$A52,'S1'!$E$6:$E$32,"Ambos")+COUNTIFS('S2'!$B$6:$B$23,$A52,'S2'!$E$6:$E$23,"Víctor")+COUNTIFS('S2'!$B$6:$B$23,$A52,'S2'!$E$6:$E$23,"Ambos")+COUNTIFS('S3'!$B$6:$B$24,$A52,'S3'!$E$6:$E$24,"Víctor")+COUNTIFS('S3'!$B$6:$B$24,$A52,'S3'!$E$6:$E$24,"Ambos")+COUNTIFS('S4'!$B$6:$B$22,$A52,'S4'!$E$6:$E$22,"Víctor")+COUNTIFS('S4'!$B$6:$B$22,$A52,'S4'!$E$6:$E$22,"Ambos")+COUNTIFS('S5'!$B$6:$B$20,$A52,'S5'!$E$6:$E$20,"Víctor")+COUNTIFS('S5'!$B$6:$B$20,$A52,'S5'!$E$6:$E$20,"Ambos")+COUNTIFS('S6'!$B$6:$B$17,$A52,'S6'!$E$6:$E$17,"Víctor")+COUNTIFS('S6'!$B$6:$B$17,$A52,'S6'!$E$6:$E$17,"Ambos")+COUNTIFS('S7'!$B$6:$B$19,$A52,'S7'!$E$6:$E$19,"Víctor")+COUNTIFS('S7'!$B$6:$B$19,$A52,'S7'!$E$6:$E$19,"Ambos")+COUNTIFS('S8'!$B$6:$B$23,$A52,'S8'!$E$6:$E$23,"Víctor")+COUNTIFS('S8'!$B$6:$B$23,$A52,'S8'!$E$6:$E$23,"Ambos")+COUNTIFS('S9'!$B$6:$B$15,$A52,'S9'!$E$6:$E$15,"Víctor")+COUNTIFS('S9'!$B$6:$B$15,$A52,'S9'!$E$6:$E$15,"Ambos")+COUNTIFS('S10'!$B$6:$B$13,$A52,'S10'!$E$6:$E$13,"Víctor")+COUNTIFS('S10'!$B$6:$B$13,$A52,'S10'!$E$6:$E$13,"Ambos")+COUNTIFS('Holgura'!$B$6:$B$11,$A52,'Holgura'!$E$6:$E$11,"Víctor")+COUNTIFS('Holgura'!$B$6:$B$11,$A52,'Holgura'!$E$6:$E$11,"Ambos")+COUNTIFS('Entrega'!$B$6:$B$9,$A52,'Entrega'!$E$6:$E$9,"Víctor")+COUNTIFS('Entrega'!$B$6:$B$9,$A52,'Entrega'!$E$6:$E$9,"Ambos")+COUNTIFS('Defensa'!$B$6:$B$10,$A52,'Defensa'!$E$6:$E$10,"Víctor")+COUNTIFS('Defensa'!$B$6:$B$10,$A52,'Defensa'!$E$6:$E$10,"Ambos")</f>
         <v/>
       </c>
       <c r="G52" s="21">
-        <f>COUNTIFS('S1'!$B$6:$B$32,$A52,'S1'!$E$6:$E$32,"Diego")+COUNTIFS('S1'!$B$6:$B$32,$A52,'S1'!$E$6:$E$32,"Ambos")+COUNTIFS('S2'!$B$6:$B$23,$A52,'S2'!$E$6:$E$23,"Diego")+COUNTIFS('S2'!$B$6:$B$23,$A52,'S2'!$E$6:$E$23,"Ambos")+COUNTIFS('S3'!$B$6:$B$19,$A52,'S3'!$E$6:$E$19,"Diego")+COUNTIFS('S3'!$B$6:$B$19,$A52,'S3'!$E$6:$E$19,"Ambos")+COUNTIFS('S4'!$B$6:$B$20,$A52,'S4'!$E$6:$E$20,"Diego")+COUNTIFS('S4'!$B$6:$B$20,$A52,'S4'!$E$6:$E$20,"Ambos")+COUNTIFS('S5'!$B$6:$B$20,$A52,'S5'!$E$6:$E$20,"Diego")+COUNTIFS('S5'!$B$6:$B$20,$A52,'S5'!$E$6:$E$20,"Ambos")+COUNTIFS('S6'!$B$6:$B$17,$A52,'S6'!$E$6:$E$17,"Diego")+COUNTIFS('S6'!$B$6:$B$17,$A52,'S6'!$E$6:$E$17,"Ambos")+COUNTIFS('S7'!$B$6:$B$19,$A52,'S7'!$E$6:$E$19,"Diego")+COUNTIFS('S7'!$B$6:$B$19,$A52,'S7'!$E$6:$E$19,"Ambos")+COUNTIFS('S8'!$B$6:$B$23,$A52,'S8'!$E$6:$E$23,"Diego")+COUNTIFS('S8'!$B$6:$B$23,$A52,'S8'!$E$6:$E$23,"Ambos")+COUNTIFS('S9'!$B$6:$B$15,$A52,'S9'!$E$6:$E$15,"Diego")+COUNTIFS('S9'!$B$6:$B$15,$A52,'S9'!$E$6:$E$15,"Ambos")+COUNTIFS('S10'!$B$6:$B$13,$A52,'S10'!$E$6:$E$13,"Diego")+COUNTIFS('S10'!$B$6:$B$13,$A52,'S10'!$E$6:$E$13,"Ambos")+COUNTIFS('Holgura'!$B$6:$B$11,$A52,'Holgura'!$E$6:$E$11,"Diego")+COUNTIFS('Holgura'!$B$6:$B$11,$A52,'Holgura'!$E$6:$E$11,"Ambos")+COUNTIFS('Entrega'!$B$6:$B$9,$A52,'Entrega'!$E$6:$E$9,"Diego")+COUNTIFS('Entrega'!$B$6:$B$9,$A52,'Entrega'!$E$6:$E$9,"Ambos")+COUNTIFS('Defensa'!$B$6:$B$10,$A52,'Defensa'!$E$6:$E$10,"Diego")+COUNTIFS('Defensa'!$B$6:$B$10,$A52,'Defensa'!$E$6:$E$10,"Ambos")</f>
+        <f>COUNTIFS('S1'!$B$6:$B$32,$A52,'S1'!$E$6:$E$32,"Diego")+COUNTIFS('S1'!$B$6:$B$32,$A52,'S1'!$E$6:$E$32,"Ambos")+COUNTIFS('S2'!$B$6:$B$23,$A52,'S2'!$E$6:$E$23,"Diego")+COUNTIFS('S2'!$B$6:$B$23,$A52,'S2'!$E$6:$E$23,"Ambos")+COUNTIFS('S3'!$B$6:$B$24,$A52,'S3'!$E$6:$E$24,"Diego")+COUNTIFS('S3'!$B$6:$B$24,$A52,'S3'!$E$6:$E$24,"Ambos")+COUNTIFS('S4'!$B$6:$B$22,$A52,'S4'!$E$6:$E$22,"Diego")+COUNTIFS('S4'!$B$6:$B$22,$A52,'S4'!$E$6:$E$22,"Ambos")+COUNTIFS('S5'!$B$6:$B$20,$A52,'S5'!$E$6:$E$20,"Diego")+COUNTIFS('S5'!$B$6:$B$20,$A52,'S5'!$E$6:$E$20,"Ambos")+COUNTIFS('S6'!$B$6:$B$17,$A52,'S6'!$E$6:$E$17,"Diego")+COUNTIFS('S6'!$B$6:$B$17,$A52,'S6'!$E$6:$E$17,"Ambos")+COUNTIFS('S7'!$B$6:$B$19,$A52,'S7'!$E$6:$E$19,"Diego")+COUNTIFS('S7'!$B$6:$B$19,$A52,'S7'!$E$6:$E$19,"Ambos")+COUNTIFS('S8'!$B$6:$B$23,$A52,'S8'!$E$6:$E$23,"Diego")+COUNTIFS('S8'!$B$6:$B$23,$A52,'S8'!$E$6:$E$23,"Ambos")+COUNTIFS('S9'!$B$6:$B$15,$A52,'S9'!$E$6:$E$15,"Diego")+COUNTIFS('S9'!$B$6:$B$15,$A52,'S9'!$E$6:$E$15,"Ambos")+COUNTIFS('S10'!$B$6:$B$13,$A52,'S10'!$E$6:$E$13,"Diego")+COUNTIFS('S10'!$B$6:$B$13,$A52,'S10'!$E$6:$E$13,"Ambos")+COUNTIFS('Holgura'!$B$6:$B$11,$A52,'Holgura'!$E$6:$E$11,"Diego")+COUNTIFS('Holgura'!$B$6:$B$11,$A52,'Holgura'!$E$6:$E$11,"Ambos")+COUNTIFS('Entrega'!$B$6:$B$9,$A52,'Entrega'!$E$6:$E$9,"Diego")+COUNTIFS('Entrega'!$B$6:$B$9,$A52,'Entrega'!$E$6:$E$9,"Ambos")+COUNTIFS('Defensa'!$B$6:$B$10,$A52,'Defensa'!$E$6:$E$10,"Diego")+COUNTIFS('Defensa'!$B$6:$B$10,$A52,'Defensa'!$E$6:$E$10,"Ambos")</f>
         <v/>
       </c>
     </row>
@@ -10072,19 +10093,19 @@
         <v/>
       </c>
       <c r="D53" s="21">
-        <f>SUMIFS('S1'!$I$6:$I$32,'S1'!$B$6:$B$32,$A53,'S1'!$E$6:$E$32,"Víctor")+SUMIFS('S1'!$I$6:$I$32,'S1'!$B$6:$B$32,$A53,'S1'!$E$6:$E$32,"Ambos")+SUMIFS('S2'!$I$6:$I$23,'S2'!$B$6:$B$23,$A53,'S2'!$E$6:$E$23,"Víctor")+SUMIFS('S2'!$I$6:$I$23,'S2'!$B$6:$B$23,$A53,'S2'!$E$6:$E$23,"Ambos")+SUMIFS('S3'!$I$6:$I$19,'S3'!$B$6:$B$19,$A53,'S3'!$E$6:$E$19,"Víctor")+SUMIFS('S3'!$I$6:$I$19,'S3'!$B$6:$B$19,$A53,'S3'!$E$6:$E$19,"Ambos")+SUMIFS('S4'!$I$6:$I$20,'S4'!$B$6:$B$20,$A53,'S4'!$E$6:$E$20,"Víctor")+SUMIFS('S4'!$I$6:$I$20,'S4'!$B$6:$B$20,$A53,'S4'!$E$6:$E$20,"Ambos")+SUMIFS('S5'!$I$6:$I$20,'S5'!$B$6:$B$20,$A53,'S5'!$E$6:$E$20,"Víctor")+SUMIFS('S5'!$I$6:$I$20,'S5'!$B$6:$B$20,$A53,'S5'!$E$6:$E$20,"Ambos")+SUMIFS('S6'!$I$6:$I$17,'S6'!$B$6:$B$17,$A53,'S6'!$E$6:$E$17,"Víctor")+SUMIFS('S6'!$I$6:$I$17,'S6'!$B$6:$B$17,$A53,'S6'!$E$6:$E$17,"Ambos")+SUMIFS('S7'!$I$6:$I$19,'S7'!$B$6:$B$19,$A53,'S7'!$E$6:$E$19,"Víctor")+SUMIFS('S7'!$I$6:$I$19,'S7'!$B$6:$B$19,$A53,'S7'!$E$6:$E$19,"Ambos")+SUMIFS('S8'!$I$6:$I$23,'S8'!$B$6:$B$23,$A53,'S8'!$E$6:$E$23,"Víctor")+SUMIFS('S8'!$I$6:$I$23,'S8'!$B$6:$B$23,$A53,'S8'!$E$6:$E$23,"Ambos")+SUMIFS('S9'!$I$6:$I$15,'S9'!$B$6:$B$15,$A53,'S9'!$E$6:$E$15,"Víctor")+SUMIFS('S9'!$I$6:$I$15,'S9'!$B$6:$B$15,$A53,'S9'!$E$6:$E$15,"Ambos")+SUMIFS('S10'!$I$6:$I$13,'S10'!$B$6:$B$13,$A53,'S10'!$E$6:$E$13,"Víctor")+SUMIFS('S10'!$I$6:$I$13,'S10'!$B$6:$B$13,$A53,'S10'!$E$6:$E$13,"Ambos")+SUMIFS('Holgura'!$I$6:$I$11,'Holgura'!$B$6:$B$11,$A53,'Holgura'!$E$6:$E$11,"Víctor")+SUMIFS('Holgura'!$I$6:$I$11,'Holgura'!$B$6:$B$11,$A53,'Holgura'!$E$6:$E$11,"Ambos")+SUMIFS('Entrega'!$I$6:$I$9,'Entrega'!$B$6:$B$9,$A53,'Entrega'!$E$6:$E$9,"Víctor")+SUMIFS('Entrega'!$I$6:$I$9,'Entrega'!$B$6:$B$9,$A53,'Entrega'!$E$6:$E$9,"Ambos")+SUMIFS('Defensa'!$I$6:$I$10,'Defensa'!$B$6:$B$10,$A53,'Defensa'!$E$6:$E$10,"Víctor")+SUMIFS('Defensa'!$I$6:$I$10,'Defensa'!$B$6:$B$10,$A53,'Defensa'!$E$6:$E$10,"Ambos")</f>
+        <f>SUMIFS('S1'!$I$6:$I$32,'S1'!$B$6:$B$32,$A53,'S1'!$E$6:$E$32,"Víctor")+SUMIFS('S1'!$I$6:$I$32,'S1'!$B$6:$B$32,$A53,'S1'!$E$6:$E$32,"Ambos")+SUMIFS('S2'!$I$6:$I$23,'S2'!$B$6:$B$23,$A53,'S2'!$E$6:$E$23,"Víctor")+SUMIFS('S2'!$I$6:$I$23,'S2'!$B$6:$B$23,$A53,'S2'!$E$6:$E$23,"Ambos")+SUMIFS('S3'!$I$6:$I$24,'S3'!$B$6:$B$24,$A53,'S3'!$E$6:$E$24,"Víctor")+SUMIFS('S3'!$I$6:$I$24,'S3'!$B$6:$B$24,$A53,'S3'!$E$6:$E$24,"Ambos")+SUMIFS('S4'!$I$6:$I$22,'S4'!$B$6:$B$22,$A53,'S4'!$E$6:$E$22,"Víctor")+SUMIFS('S4'!$I$6:$I$22,'S4'!$B$6:$B$22,$A53,'S4'!$E$6:$E$22,"Ambos")+SUMIFS('S5'!$I$6:$I$20,'S5'!$B$6:$B$20,$A53,'S5'!$E$6:$E$20,"Víctor")+SUMIFS('S5'!$I$6:$I$20,'S5'!$B$6:$B$20,$A53,'S5'!$E$6:$E$20,"Ambos")+SUMIFS('S6'!$I$6:$I$17,'S6'!$B$6:$B$17,$A53,'S6'!$E$6:$E$17,"Víctor")+SUMIFS('S6'!$I$6:$I$17,'S6'!$B$6:$B$17,$A53,'S6'!$E$6:$E$17,"Ambos")+SUMIFS('S7'!$I$6:$I$19,'S7'!$B$6:$B$19,$A53,'S7'!$E$6:$E$19,"Víctor")+SUMIFS('S7'!$I$6:$I$19,'S7'!$B$6:$B$19,$A53,'S7'!$E$6:$E$19,"Ambos")+SUMIFS('S8'!$I$6:$I$23,'S8'!$B$6:$B$23,$A53,'S8'!$E$6:$E$23,"Víctor")+SUMIFS('S8'!$I$6:$I$23,'S8'!$B$6:$B$23,$A53,'S8'!$E$6:$E$23,"Ambos")+SUMIFS('S9'!$I$6:$I$15,'S9'!$B$6:$B$15,$A53,'S9'!$E$6:$E$15,"Víctor")+SUMIFS('S9'!$I$6:$I$15,'S9'!$B$6:$B$15,$A53,'S9'!$E$6:$E$15,"Ambos")+SUMIFS('S10'!$I$6:$I$13,'S10'!$B$6:$B$13,$A53,'S10'!$E$6:$E$13,"Víctor")+SUMIFS('S10'!$I$6:$I$13,'S10'!$B$6:$B$13,$A53,'S10'!$E$6:$E$13,"Ambos")+SUMIFS('Holgura'!$I$6:$I$11,'Holgura'!$B$6:$B$11,$A53,'Holgura'!$E$6:$E$11,"Víctor")+SUMIFS('Holgura'!$I$6:$I$11,'Holgura'!$B$6:$B$11,$A53,'Holgura'!$E$6:$E$11,"Ambos")+SUMIFS('Entrega'!$I$6:$I$9,'Entrega'!$B$6:$B$9,$A53,'Entrega'!$E$6:$E$9,"Víctor")+SUMIFS('Entrega'!$I$6:$I$9,'Entrega'!$B$6:$B$9,$A53,'Entrega'!$E$6:$E$9,"Ambos")+SUMIFS('Defensa'!$I$6:$I$10,'Defensa'!$B$6:$B$10,$A53,'Defensa'!$E$6:$E$10,"Víctor")+SUMIFS('Defensa'!$I$6:$I$10,'Defensa'!$B$6:$B$10,$A53,'Defensa'!$E$6:$E$10,"Ambos")</f>
         <v/>
       </c>
       <c r="E53" s="21">
-        <f>SUMIFS('S1'!$I$6:$I$32,'S1'!$B$6:$B$32,$A53,'S1'!$E$6:$E$32,"Diego")+SUMIFS('S1'!$I$6:$I$32,'S1'!$B$6:$B$32,$A53,'S1'!$E$6:$E$32,"Ambos")+SUMIFS('S2'!$I$6:$I$23,'S2'!$B$6:$B$23,$A53,'S2'!$E$6:$E$23,"Diego")+SUMIFS('S2'!$I$6:$I$23,'S2'!$B$6:$B$23,$A53,'S2'!$E$6:$E$23,"Ambos")+SUMIFS('S3'!$I$6:$I$19,'S3'!$B$6:$B$19,$A53,'S3'!$E$6:$E$19,"Diego")+SUMIFS('S3'!$I$6:$I$19,'S3'!$B$6:$B$19,$A53,'S3'!$E$6:$E$19,"Ambos")+SUMIFS('S4'!$I$6:$I$20,'S4'!$B$6:$B$20,$A53,'S4'!$E$6:$E$20,"Diego")+SUMIFS('S4'!$I$6:$I$20,'S4'!$B$6:$B$20,$A53,'S4'!$E$6:$E$20,"Ambos")+SUMIFS('S5'!$I$6:$I$20,'S5'!$B$6:$B$20,$A53,'S5'!$E$6:$E$20,"Diego")+SUMIFS('S5'!$I$6:$I$20,'S5'!$B$6:$B$20,$A53,'S5'!$E$6:$E$20,"Ambos")+SUMIFS('S6'!$I$6:$I$17,'S6'!$B$6:$B$17,$A53,'S6'!$E$6:$E$17,"Diego")+SUMIFS('S6'!$I$6:$I$17,'S6'!$B$6:$B$17,$A53,'S6'!$E$6:$E$17,"Ambos")+SUMIFS('S7'!$I$6:$I$19,'S7'!$B$6:$B$19,$A53,'S7'!$E$6:$E$19,"Diego")+SUMIFS('S7'!$I$6:$I$19,'S7'!$B$6:$B$19,$A53,'S7'!$E$6:$E$19,"Ambos")+SUMIFS('S8'!$I$6:$I$23,'S8'!$B$6:$B$23,$A53,'S8'!$E$6:$E$23,"Diego")+SUMIFS('S8'!$I$6:$I$23,'S8'!$B$6:$B$23,$A53,'S8'!$E$6:$E$23,"Ambos")+SUMIFS('S9'!$I$6:$I$15,'S9'!$B$6:$B$15,$A53,'S9'!$E$6:$E$15,"Diego")+SUMIFS('S9'!$I$6:$I$15,'S9'!$B$6:$B$15,$A53,'S9'!$E$6:$E$15,"Ambos")+SUMIFS('S10'!$I$6:$I$13,'S10'!$B$6:$B$13,$A53,'S10'!$E$6:$E$13,"Diego")+SUMIFS('S10'!$I$6:$I$13,'S10'!$B$6:$B$13,$A53,'S10'!$E$6:$E$13,"Ambos")+SUMIFS('Holgura'!$I$6:$I$11,'Holgura'!$B$6:$B$11,$A53,'Holgura'!$E$6:$E$11,"Diego")+SUMIFS('Holgura'!$I$6:$I$11,'Holgura'!$B$6:$B$11,$A53,'Holgura'!$E$6:$E$11,"Ambos")+SUMIFS('Entrega'!$I$6:$I$9,'Entrega'!$B$6:$B$9,$A53,'Entrega'!$E$6:$E$9,"Diego")+SUMIFS('Entrega'!$I$6:$I$9,'Entrega'!$B$6:$B$9,$A53,'Entrega'!$E$6:$E$9,"Ambos")+SUMIFS('Defensa'!$I$6:$I$10,'Defensa'!$B$6:$B$10,$A53,'Defensa'!$E$6:$E$10,"Diego")+SUMIFS('Defensa'!$I$6:$I$10,'Defensa'!$B$6:$B$10,$A53,'Defensa'!$E$6:$E$10,"Ambos")</f>
+        <f>SUMIFS('S1'!$I$6:$I$32,'S1'!$B$6:$B$32,$A53,'S1'!$E$6:$E$32,"Diego")+SUMIFS('S1'!$I$6:$I$32,'S1'!$B$6:$B$32,$A53,'S1'!$E$6:$E$32,"Ambos")+SUMIFS('S2'!$I$6:$I$23,'S2'!$B$6:$B$23,$A53,'S2'!$E$6:$E$23,"Diego")+SUMIFS('S2'!$I$6:$I$23,'S2'!$B$6:$B$23,$A53,'S2'!$E$6:$E$23,"Ambos")+SUMIFS('S3'!$I$6:$I$24,'S3'!$B$6:$B$24,$A53,'S3'!$E$6:$E$24,"Diego")+SUMIFS('S3'!$I$6:$I$24,'S3'!$B$6:$B$24,$A53,'S3'!$E$6:$E$24,"Ambos")+SUMIFS('S4'!$I$6:$I$22,'S4'!$B$6:$B$22,$A53,'S4'!$E$6:$E$22,"Diego")+SUMIFS('S4'!$I$6:$I$22,'S4'!$B$6:$B$22,$A53,'S4'!$E$6:$E$22,"Ambos")+SUMIFS('S5'!$I$6:$I$20,'S5'!$B$6:$B$20,$A53,'S5'!$E$6:$E$20,"Diego")+SUMIFS('S5'!$I$6:$I$20,'S5'!$B$6:$B$20,$A53,'S5'!$E$6:$E$20,"Ambos")+SUMIFS('S6'!$I$6:$I$17,'S6'!$B$6:$B$17,$A53,'S6'!$E$6:$E$17,"Diego")+SUMIFS('S6'!$I$6:$I$17,'S6'!$B$6:$B$17,$A53,'S6'!$E$6:$E$17,"Ambos")+SUMIFS('S7'!$I$6:$I$19,'S7'!$B$6:$B$19,$A53,'S7'!$E$6:$E$19,"Diego")+SUMIFS('S7'!$I$6:$I$19,'S7'!$B$6:$B$19,$A53,'S7'!$E$6:$E$19,"Ambos")+SUMIFS('S8'!$I$6:$I$23,'S8'!$B$6:$B$23,$A53,'S8'!$E$6:$E$23,"Diego")+SUMIFS('S8'!$I$6:$I$23,'S8'!$B$6:$B$23,$A53,'S8'!$E$6:$E$23,"Ambos")+SUMIFS('S9'!$I$6:$I$15,'S9'!$B$6:$B$15,$A53,'S9'!$E$6:$E$15,"Diego")+SUMIFS('S9'!$I$6:$I$15,'S9'!$B$6:$B$15,$A53,'S9'!$E$6:$E$15,"Ambos")+SUMIFS('S10'!$I$6:$I$13,'S10'!$B$6:$B$13,$A53,'S10'!$E$6:$E$13,"Diego")+SUMIFS('S10'!$I$6:$I$13,'S10'!$B$6:$B$13,$A53,'S10'!$E$6:$E$13,"Ambos")+SUMIFS('Holgura'!$I$6:$I$11,'Holgura'!$B$6:$B$11,$A53,'Holgura'!$E$6:$E$11,"Diego")+SUMIFS('Holgura'!$I$6:$I$11,'Holgura'!$B$6:$B$11,$A53,'Holgura'!$E$6:$E$11,"Ambos")+SUMIFS('Entrega'!$I$6:$I$9,'Entrega'!$B$6:$B$9,$A53,'Entrega'!$E$6:$E$9,"Diego")+SUMIFS('Entrega'!$I$6:$I$9,'Entrega'!$B$6:$B$9,$A53,'Entrega'!$E$6:$E$9,"Ambos")+SUMIFS('Defensa'!$I$6:$I$10,'Defensa'!$B$6:$B$10,$A53,'Defensa'!$E$6:$E$10,"Diego")+SUMIFS('Defensa'!$I$6:$I$10,'Defensa'!$B$6:$B$10,$A53,'Defensa'!$E$6:$E$10,"Ambos")</f>
         <v/>
       </c>
       <c r="F53" s="21">
-        <f>COUNTIFS('S1'!$B$6:$B$32,$A53,'S1'!$E$6:$E$32,"Víctor")+COUNTIFS('S1'!$B$6:$B$32,$A53,'S1'!$E$6:$E$32,"Ambos")+COUNTIFS('S2'!$B$6:$B$23,$A53,'S2'!$E$6:$E$23,"Víctor")+COUNTIFS('S2'!$B$6:$B$23,$A53,'S2'!$E$6:$E$23,"Ambos")+COUNTIFS('S3'!$B$6:$B$19,$A53,'S3'!$E$6:$E$19,"Víctor")+COUNTIFS('S3'!$B$6:$B$19,$A53,'S3'!$E$6:$E$19,"Ambos")+COUNTIFS('S4'!$B$6:$B$20,$A53,'S4'!$E$6:$E$20,"Víctor")+COUNTIFS('S4'!$B$6:$B$20,$A53,'S4'!$E$6:$E$20,"Ambos")+COUNTIFS('S5'!$B$6:$B$20,$A53,'S5'!$E$6:$E$20,"Víctor")+COUNTIFS('S5'!$B$6:$B$20,$A53,'S5'!$E$6:$E$20,"Ambos")+COUNTIFS('S6'!$B$6:$B$17,$A53,'S6'!$E$6:$E$17,"Víctor")+COUNTIFS('S6'!$B$6:$B$17,$A53,'S6'!$E$6:$E$17,"Ambos")+COUNTIFS('S7'!$B$6:$B$19,$A53,'S7'!$E$6:$E$19,"Víctor")+COUNTIFS('S7'!$B$6:$B$19,$A53,'S7'!$E$6:$E$19,"Ambos")+COUNTIFS('S8'!$B$6:$B$23,$A53,'S8'!$E$6:$E$23,"Víctor")+COUNTIFS('S8'!$B$6:$B$23,$A53,'S8'!$E$6:$E$23,"Ambos")+COUNTIFS('S9'!$B$6:$B$15,$A53,'S9'!$E$6:$E$15,"Víctor")+COUNTIFS('S9'!$B$6:$B$15,$A53,'S9'!$E$6:$E$15,"Ambos")+COUNTIFS('S10'!$B$6:$B$13,$A53,'S10'!$E$6:$E$13,"Víctor")+COUNTIFS('S10'!$B$6:$B$13,$A53,'S10'!$E$6:$E$13,"Ambos")+COUNTIFS('Holgura'!$B$6:$B$11,$A53,'Holgura'!$E$6:$E$11,"Víctor")+COUNTIFS('Holgura'!$B$6:$B$11,$A53,'Holgura'!$E$6:$E$11,"Ambos")+COUNTIFS('Entrega'!$B$6:$B$9,$A53,'Entrega'!$E$6:$E$9,"Víctor")+COUNTIFS('Entrega'!$B$6:$B$9,$A53,'Entrega'!$E$6:$E$9,"Ambos")+COUNTIFS('Defensa'!$B$6:$B$10,$A53,'Defensa'!$E$6:$E$10,"Víctor")+COUNTIFS('Defensa'!$B$6:$B$10,$A53,'Defensa'!$E$6:$E$10,"Ambos")</f>
+        <f>COUNTIFS('S1'!$B$6:$B$32,$A53,'S1'!$E$6:$E$32,"Víctor")+COUNTIFS('S1'!$B$6:$B$32,$A53,'S1'!$E$6:$E$32,"Ambos")+COUNTIFS('S2'!$B$6:$B$23,$A53,'S2'!$E$6:$E$23,"Víctor")+COUNTIFS('S2'!$B$6:$B$23,$A53,'S2'!$E$6:$E$23,"Ambos")+COUNTIFS('S3'!$B$6:$B$24,$A53,'S3'!$E$6:$E$24,"Víctor")+COUNTIFS('S3'!$B$6:$B$24,$A53,'S3'!$E$6:$E$24,"Ambos")+COUNTIFS('S4'!$B$6:$B$22,$A53,'S4'!$E$6:$E$22,"Víctor")+COUNTIFS('S4'!$B$6:$B$22,$A53,'S4'!$E$6:$E$22,"Ambos")+COUNTIFS('S5'!$B$6:$B$20,$A53,'S5'!$E$6:$E$20,"Víctor")+COUNTIFS('S5'!$B$6:$B$20,$A53,'S5'!$E$6:$E$20,"Ambos")+COUNTIFS('S6'!$B$6:$B$17,$A53,'S6'!$E$6:$E$17,"Víctor")+COUNTIFS('S6'!$B$6:$B$17,$A53,'S6'!$E$6:$E$17,"Ambos")+COUNTIFS('S7'!$B$6:$B$19,$A53,'S7'!$E$6:$E$19,"Víctor")+COUNTIFS('S7'!$B$6:$B$19,$A53,'S7'!$E$6:$E$19,"Ambos")+COUNTIFS('S8'!$B$6:$B$23,$A53,'S8'!$E$6:$E$23,"Víctor")+COUNTIFS('S8'!$B$6:$B$23,$A53,'S8'!$E$6:$E$23,"Ambos")+COUNTIFS('S9'!$B$6:$B$15,$A53,'S9'!$E$6:$E$15,"Víctor")+COUNTIFS('S9'!$B$6:$B$15,$A53,'S9'!$E$6:$E$15,"Ambos")+COUNTIFS('S10'!$B$6:$B$13,$A53,'S10'!$E$6:$E$13,"Víctor")+COUNTIFS('S10'!$B$6:$B$13,$A53,'S10'!$E$6:$E$13,"Ambos")+COUNTIFS('Holgura'!$B$6:$B$11,$A53,'Holgura'!$E$6:$E$11,"Víctor")+COUNTIFS('Holgura'!$B$6:$B$11,$A53,'Holgura'!$E$6:$E$11,"Ambos")+COUNTIFS('Entrega'!$B$6:$B$9,$A53,'Entrega'!$E$6:$E$9,"Víctor")+COUNTIFS('Entrega'!$B$6:$B$9,$A53,'Entrega'!$E$6:$E$9,"Ambos")+COUNTIFS('Defensa'!$B$6:$B$10,$A53,'Defensa'!$E$6:$E$10,"Víctor")+COUNTIFS('Defensa'!$B$6:$B$10,$A53,'Defensa'!$E$6:$E$10,"Ambos")</f>
         <v/>
       </c>
       <c r="G53" s="21">
-        <f>COUNTIFS('S1'!$B$6:$B$32,$A53,'S1'!$E$6:$E$32,"Diego")+COUNTIFS('S1'!$B$6:$B$32,$A53,'S1'!$E$6:$E$32,"Ambos")+COUNTIFS('S2'!$B$6:$B$23,$A53,'S2'!$E$6:$E$23,"Diego")+COUNTIFS('S2'!$B$6:$B$23,$A53,'S2'!$E$6:$E$23,"Ambos")+COUNTIFS('S3'!$B$6:$B$19,$A53,'S3'!$E$6:$E$19,"Diego")+COUNTIFS('S3'!$B$6:$B$19,$A53,'S3'!$E$6:$E$19,"Ambos")+COUNTIFS('S4'!$B$6:$B$20,$A53,'S4'!$E$6:$E$20,"Diego")+COUNTIFS('S4'!$B$6:$B$20,$A53,'S4'!$E$6:$E$20,"Ambos")+COUNTIFS('S5'!$B$6:$B$20,$A53,'S5'!$E$6:$E$20,"Diego")+COUNTIFS('S5'!$B$6:$B$20,$A53,'S5'!$E$6:$E$20,"Ambos")+COUNTIFS('S6'!$B$6:$B$17,$A53,'S6'!$E$6:$E$17,"Diego")+COUNTIFS('S6'!$B$6:$B$17,$A53,'S6'!$E$6:$E$17,"Ambos")+COUNTIFS('S7'!$B$6:$B$19,$A53,'S7'!$E$6:$E$19,"Diego")+COUNTIFS('S7'!$B$6:$B$19,$A53,'S7'!$E$6:$E$19,"Ambos")+COUNTIFS('S8'!$B$6:$B$23,$A53,'S8'!$E$6:$E$23,"Diego")+COUNTIFS('S8'!$B$6:$B$23,$A53,'S8'!$E$6:$E$23,"Ambos")+COUNTIFS('S9'!$B$6:$B$15,$A53,'S9'!$E$6:$E$15,"Diego")+COUNTIFS('S9'!$B$6:$B$15,$A53,'S9'!$E$6:$E$15,"Ambos")+COUNTIFS('S10'!$B$6:$B$13,$A53,'S10'!$E$6:$E$13,"Diego")+COUNTIFS('S10'!$B$6:$B$13,$A53,'S10'!$E$6:$E$13,"Ambos")+COUNTIFS('Holgura'!$B$6:$B$11,$A53,'Holgura'!$E$6:$E$11,"Diego")+COUNTIFS('Holgura'!$B$6:$B$11,$A53,'Holgura'!$E$6:$E$11,"Ambos")+COUNTIFS('Entrega'!$B$6:$B$9,$A53,'Entrega'!$E$6:$E$9,"Diego")+COUNTIFS('Entrega'!$B$6:$B$9,$A53,'Entrega'!$E$6:$E$9,"Ambos")+COUNTIFS('Defensa'!$B$6:$B$10,$A53,'Defensa'!$E$6:$E$10,"Diego")+COUNTIFS('Defensa'!$B$6:$B$10,$A53,'Defensa'!$E$6:$E$10,"Ambos")</f>
+        <f>COUNTIFS('S1'!$B$6:$B$32,$A53,'S1'!$E$6:$E$32,"Diego")+COUNTIFS('S1'!$B$6:$B$32,$A53,'S1'!$E$6:$E$32,"Ambos")+COUNTIFS('S2'!$B$6:$B$23,$A53,'S2'!$E$6:$E$23,"Diego")+COUNTIFS('S2'!$B$6:$B$23,$A53,'S2'!$E$6:$E$23,"Ambos")+COUNTIFS('S3'!$B$6:$B$24,$A53,'S3'!$E$6:$E$24,"Diego")+COUNTIFS('S3'!$B$6:$B$24,$A53,'S3'!$E$6:$E$24,"Ambos")+COUNTIFS('S4'!$B$6:$B$22,$A53,'S4'!$E$6:$E$22,"Diego")+COUNTIFS('S4'!$B$6:$B$22,$A53,'S4'!$E$6:$E$22,"Ambos")+COUNTIFS('S5'!$B$6:$B$20,$A53,'S5'!$E$6:$E$20,"Diego")+COUNTIFS('S5'!$B$6:$B$20,$A53,'S5'!$E$6:$E$20,"Ambos")+COUNTIFS('S6'!$B$6:$B$17,$A53,'S6'!$E$6:$E$17,"Diego")+COUNTIFS('S6'!$B$6:$B$17,$A53,'S6'!$E$6:$E$17,"Ambos")+COUNTIFS('S7'!$B$6:$B$19,$A53,'S7'!$E$6:$E$19,"Diego")+COUNTIFS('S7'!$B$6:$B$19,$A53,'S7'!$E$6:$E$19,"Ambos")+COUNTIFS('S8'!$B$6:$B$23,$A53,'S8'!$E$6:$E$23,"Diego")+COUNTIFS('S8'!$B$6:$B$23,$A53,'S8'!$E$6:$E$23,"Ambos")+COUNTIFS('S9'!$B$6:$B$15,$A53,'S9'!$E$6:$E$15,"Diego")+COUNTIFS('S9'!$B$6:$B$15,$A53,'S9'!$E$6:$E$15,"Ambos")+COUNTIFS('S10'!$B$6:$B$13,$A53,'S10'!$E$6:$E$13,"Diego")+COUNTIFS('S10'!$B$6:$B$13,$A53,'S10'!$E$6:$E$13,"Ambos")+COUNTIFS('Holgura'!$B$6:$B$11,$A53,'Holgura'!$E$6:$E$11,"Diego")+COUNTIFS('Holgura'!$B$6:$B$11,$A53,'Holgura'!$E$6:$E$11,"Ambos")+COUNTIFS('Entrega'!$B$6:$B$9,$A53,'Entrega'!$E$6:$E$9,"Diego")+COUNTIFS('Entrega'!$B$6:$B$9,$A53,'Entrega'!$E$6:$E$9,"Ambos")+COUNTIFS('Defensa'!$B$6:$B$10,$A53,'Defensa'!$E$6:$E$10,"Diego")+COUNTIFS('Defensa'!$B$6:$B$10,$A53,'Defensa'!$E$6:$E$10,"Ambos")</f>
         <v/>
       </c>
     </row>
@@ -10101,19 +10122,19 @@
         <v/>
       </c>
       <c r="D54" s="21">
-        <f>SUMIFS('S1'!$I$6:$I$32,'S1'!$B$6:$B$32,$A54,'S1'!$E$6:$E$32,"Víctor")+SUMIFS('S1'!$I$6:$I$32,'S1'!$B$6:$B$32,$A54,'S1'!$E$6:$E$32,"Ambos")+SUMIFS('S2'!$I$6:$I$23,'S2'!$B$6:$B$23,$A54,'S2'!$E$6:$E$23,"Víctor")+SUMIFS('S2'!$I$6:$I$23,'S2'!$B$6:$B$23,$A54,'S2'!$E$6:$E$23,"Ambos")+SUMIFS('S3'!$I$6:$I$19,'S3'!$B$6:$B$19,$A54,'S3'!$E$6:$E$19,"Víctor")+SUMIFS('S3'!$I$6:$I$19,'S3'!$B$6:$B$19,$A54,'S3'!$E$6:$E$19,"Ambos")+SUMIFS('S4'!$I$6:$I$20,'S4'!$B$6:$B$20,$A54,'S4'!$E$6:$E$20,"Víctor")+SUMIFS('S4'!$I$6:$I$20,'S4'!$B$6:$B$20,$A54,'S4'!$E$6:$E$20,"Ambos")+SUMIFS('S5'!$I$6:$I$20,'S5'!$B$6:$B$20,$A54,'S5'!$E$6:$E$20,"Víctor")+SUMIFS('S5'!$I$6:$I$20,'S5'!$B$6:$B$20,$A54,'S5'!$E$6:$E$20,"Ambos")+SUMIFS('S6'!$I$6:$I$17,'S6'!$B$6:$B$17,$A54,'S6'!$E$6:$E$17,"Víctor")+SUMIFS('S6'!$I$6:$I$17,'S6'!$B$6:$B$17,$A54,'S6'!$E$6:$E$17,"Ambos")+SUMIFS('S7'!$I$6:$I$19,'S7'!$B$6:$B$19,$A54,'S7'!$E$6:$E$19,"Víctor")+SUMIFS('S7'!$I$6:$I$19,'S7'!$B$6:$B$19,$A54,'S7'!$E$6:$E$19,"Ambos")+SUMIFS('S8'!$I$6:$I$23,'S8'!$B$6:$B$23,$A54,'S8'!$E$6:$E$23,"Víctor")+SUMIFS('S8'!$I$6:$I$23,'S8'!$B$6:$B$23,$A54,'S8'!$E$6:$E$23,"Ambos")+SUMIFS('S9'!$I$6:$I$15,'S9'!$B$6:$B$15,$A54,'S9'!$E$6:$E$15,"Víctor")+SUMIFS('S9'!$I$6:$I$15,'S9'!$B$6:$B$15,$A54,'S9'!$E$6:$E$15,"Ambos")+SUMIFS('S10'!$I$6:$I$13,'S10'!$B$6:$B$13,$A54,'S10'!$E$6:$E$13,"Víctor")+SUMIFS('S10'!$I$6:$I$13,'S10'!$B$6:$B$13,$A54,'S10'!$E$6:$E$13,"Ambos")+SUMIFS('Holgura'!$I$6:$I$11,'Holgura'!$B$6:$B$11,$A54,'Holgura'!$E$6:$E$11,"Víctor")+SUMIFS('Holgura'!$I$6:$I$11,'Holgura'!$B$6:$B$11,$A54,'Holgura'!$E$6:$E$11,"Ambos")+SUMIFS('Entrega'!$I$6:$I$9,'Entrega'!$B$6:$B$9,$A54,'Entrega'!$E$6:$E$9,"Víctor")+SUMIFS('Entrega'!$I$6:$I$9,'Entrega'!$B$6:$B$9,$A54,'Entrega'!$E$6:$E$9,"Ambos")+SUMIFS('Defensa'!$I$6:$I$10,'Defensa'!$B$6:$B$10,$A54,'Defensa'!$E$6:$E$10,"Víctor")+SUMIFS('Defensa'!$I$6:$I$10,'Defensa'!$B$6:$B$10,$A54,'Defensa'!$E$6:$E$10,"Ambos")</f>
+        <f>SUMIFS('S1'!$I$6:$I$32,'S1'!$B$6:$B$32,$A54,'S1'!$E$6:$E$32,"Víctor")+SUMIFS('S1'!$I$6:$I$32,'S1'!$B$6:$B$32,$A54,'S1'!$E$6:$E$32,"Ambos")+SUMIFS('S2'!$I$6:$I$23,'S2'!$B$6:$B$23,$A54,'S2'!$E$6:$E$23,"Víctor")+SUMIFS('S2'!$I$6:$I$23,'S2'!$B$6:$B$23,$A54,'S2'!$E$6:$E$23,"Ambos")+SUMIFS('S3'!$I$6:$I$24,'S3'!$B$6:$B$24,$A54,'S3'!$E$6:$E$24,"Víctor")+SUMIFS('S3'!$I$6:$I$24,'S3'!$B$6:$B$24,$A54,'S3'!$E$6:$E$24,"Ambos")+SUMIFS('S4'!$I$6:$I$22,'S4'!$B$6:$B$22,$A54,'S4'!$E$6:$E$22,"Víctor")+SUMIFS('S4'!$I$6:$I$22,'S4'!$B$6:$B$22,$A54,'S4'!$E$6:$E$22,"Ambos")+SUMIFS('S5'!$I$6:$I$20,'S5'!$B$6:$B$20,$A54,'S5'!$E$6:$E$20,"Víctor")+SUMIFS('S5'!$I$6:$I$20,'S5'!$B$6:$B$20,$A54,'S5'!$E$6:$E$20,"Ambos")+SUMIFS('S6'!$I$6:$I$17,'S6'!$B$6:$B$17,$A54,'S6'!$E$6:$E$17,"Víctor")+SUMIFS('S6'!$I$6:$I$17,'S6'!$B$6:$B$17,$A54,'S6'!$E$6:$E$17,"Ambos")+SUMIFS('S7'!$I$6:$I$19,'S7'!$B$6:$B$19,$A54,'S7'!$E$6:$E$19,"Víctor")+SUMIFS('S7'!$I$6:$I$19,'S7'!$B$6:$B$19,$A54,'S7'!$E$6:$E$19,"Ambos")+SUMIFS('S8'!$I$6:$I$23,'S8'!$B$6:$B$23,$A54,'S8'!$E$6:$E$23,"Víctor")+SUMIFS('S8'!$I$6:$I$23,'S8'!$B$6:$B$23,$A54,'S8'!$E$6:$E$23,"Ambos")+SUMIFS('S9'!$I$6:$I$15,'S9'!$B$6:$B$15,$A54,'S9'!$E$6:$E$15,"Víctor")+SUMIFS('S9'!$I$6:$I$15,'S9'!$B$6:$B$15,$A54,'S9'!$E$6:$E$15,"Ambos")+SUMIFS('S10'!$I$6:$I$13,'S10'!$B$6:$B$13,$A54,'S10'!$E$6:$E$13,"Víctor")+SUMIFS('S10'!$I$6:$I$13,'S10'!$B$6:$B$13,$A54,'S10'!$E$6:$E$13,"Ambos")+SUMIFS('Holgura'!$I$6:$I$11,'Holgura'!$B$6:$B$11,$A54,'Holgura'!$E$6:$E$11,"Víctor")+SUMIFS('Holgura'!$I$6:$I$11,'Holgura'!$B$6:$B$11,$A54,'Holgura'!$E$6:$E$11,"Ambos")+SUMIFS('Entrega'!$I$6:$I$9,'Entrega'!$B$6:$B$9,$A54,'Entrega'!$E$6:$E$9,"Víctor")+SUMIFS('Entrega'!$I$6:$I$9,'Entrega'!$B$6:$B$9,$A54,'Entrega'!$E$6:$E$9,"Ambos")+SUMIFS('Defensa'!$I$6:$I$10,'Defensa'!$B$6:$B$10,$A54,'Defensa'!$E$6:$E$10,"Víctor")+SUMIFS('Defensa'!$I$6:$I$10,'Defensa'!$B$6:$B$10,$A54,'Defensa'!$E$6:$E$10,"Ambos")</f>
         <v/>
       </c>
       <c r="E54" s="21">
-        <f>SUMIFS('S1'!$I$6:$I$32,'S1'!$B$6:$B$32,$A54,'S1'!$E$6:$E$32,"Diego")+SUMIFS('S1'!$I$6:$I$32,'S1'!$B$6:$B$32,$A54,'S1'!$E$6:$E$32,"Ambos")+SUMIFS('S2'!$I$6:$I$23,'S2'!$B$6:$B$23,$A54,'S2'!$E$6:$E$23,"Diego")+SUMIFS('S2'!$I$6:$I$23,'S2'!$B$6:$B$23,$A54,'S2'!$E$6:$E$23,"Ambos")+SUMIFS('S3'!$I$6:$I$19,'S3'!$B$6:$B$19,$A54,'S3'!$E$6:$E$19,"Diego")+SUMIFS('S3'!$I$6:$I$19,'S3'!$B$6:$B$19,$A54,'S3'!$E$6:$E$19,"Ambos")+SUMIFS('S4'!$I$6:$I$20,'S4'!$B$6:$B$20,$A54,'S4'!$E$6:$E$20,"Diego")+SUMIFS('S4'!$I$6:$I$20,'S4'!$B$6:$B$20,$A54,'S4'!$E$6:$E$20,"Ambos")+SUMIFS('S5'!$I$6:$I$20,'S5'!$B$6:$B$20,$A54,'S5'!$E$6:$E$20,"Diego")+SUMIFS('S5'!$I$6:$I$20,'S5'!$B$6:$B$20,$A54,'S5'!$E$6:$E$20,"Ambos")+SUMIFS('S6'!$I$6:$I$17,'S6'!$B$6:$B$17,$A54,'S6'!$E$6:$E$17,"Diego")+SUMIFS('S6'!$I$6:$I$17,'S6'!$B$6:$B$17,$A54,'S6'!$E$6:$E$17,"Ambos")+SUMIFS('S7'!$I$6:$I$19,'S7'!$B$6:$B$19,$A54,'S7'!$E$6:$E$19,"Diego")+SUMIFS('S7'!$I$6:$I$19,'S7'!$B$6:$B$19,$A54,'S7'!$E$6:$E$19,"Ambos")+SUMIFS('S8'!$I$6:$I$23,'S8'!$B$6:$B$23,$A54,'S8'!$E$6:$E$23,"Diego")+SUMIFS('S8'!$I$6:$I$23,'S8'!$B$6:$B$23,$A54,'S8'!$E$6:$E$23,"Ambos")+SUMIFS('S9'!$I$6:$I$15,'S9'!$B$6:$B$15,$A54,'S9'!$E$6:$E$15,"Diego")+SUMIFS('S9'!$I$6:$I$15,'S9'!$B$6:$B$15,$A54,'S9'!$E$6:$E$15,"Ambos")+SUMIFS('S10'!$I$6:$I$13,'S10'!$B$6:$B$13,$A54,'S10'!$E$6:$E$13,"Diego")+SUMIFS('S10'!$I$6:$I$13,'S10'!$B$6:$B$13,$A54,'S10'!$E$6:$E$13,"Ambos")+SUMIFS('Holgura'!$I$6:$I$11,'Holgura'!$B$6:$B$11,$A54,'Holgura'!$E$6:$E$11,"Diego")+SUMIFS('Holgura'!$I$6:$I$11,'Holgura'!$B$6:$B$11,$A54,'Holgura'!$E$6:$E$11,"Ambos")+SUMIFS('Entrega'!$I$6:$I$9,'Entrega'!$B$6:$B$9,$A54,'Entrega'!$E$6:$E$9,"Diego")+SUMIFS('Entrega'!$I$6:$I$9,'Entrega'!$B$6:$B$9,$A54,'Entrega'!$E$6:$E$9,"Ambos")+SUMIFS('Defensa'!$I$6:$I$10,'Defensa'!$B$6:$B$10,$A54,'Defensa'!$E$6:$E$10,"Diego")+SUMIFS('Defensa'!$I$6:$I$10,'Defensa'!$B$6:$B$10,$A54,'Defensa'!$E$6:$E$10,"Ambos")</f>
+        <f>SUMIFS('S1'!$I$6:$I$32,'S1'!$B$6:$B$32,$A54,'S1'!$E$6:$E$32,"Diego")+SUMIFS('S1'!$I$6:$I$32,'S1'!$B$6:$B$32,$A54,'S1'!$E$6:$E$32,"Ambos")+SUMIFS('S2'!$I$6:$I$23,'S2'!$B$6:$B$23,$A54,'S2'!$E$6:$E$23,"Diego")+SUMIFS('S2'!$I$6:$I$23,'S2'!$B$6:$B$23,$A54,'S2'!$E$6:$E$23,"Ambos")+SUMIFS('S3'!$I$6:$I$24,'S3'!$B$6:$B$24,$A54,'S3'!$E$6:$E$24,"Diego")+SUMIFS('S3'!$I$6:$I$24,'S3'!$B$6:$B$24,$A54,'S3'!$E$6:$E$24,"Ambos")+SUMIFS('S4'!$I$6:$I$22,'S4'!$B$6:$B$22,$A54,'S4'!$E$6:$E$22,"Diego")+SUMIFS('S4'!$I$6:$I$22,'S4'!$B$6:$B$22,$A54,'S4'!$E$6:$E$22,"Ambos")+SUMIFS('S5'!$I$6:$I$20,'S5'!$B$6:$B$20,$A54,'S5'!$E$6:$E$20,"Diego")+SUMIFS('S5'!$I$6:$I$20,'S5'!$B$6:$B$20,$A54,'S5'!$E$6:$E$20,"Ambos")+SUMIFS('S6'!$I$6:$I$17,'S6'!$B$6:$B$17,$A54,'S6'!$E$6:$E$17,"Diego")+SUMIFS('S6'!$I$6:$I$17,'S6'!$B$6:$B$17,$A54,'S6'!$E$6:$E$17,"Ambos")+SUMIFS('S7'!$I$6:$I$19,'S7'!$B$6:$B$19,$A54,'S7'!$E$6:$E$19,"Diego")+SUMIFS('S7'!$I$6:$I$19,'S7'!$B$6:$B$19,$A54,'S7'!$E$6:$E$19,"Ambos")+SUMIFS('S8'!$I$6:$I$23,'S8'!$B$6:$B$23,$A54,'S8'!$E$6:$E$23,"Diego")+SUMIFS('S8'!$I$6:$I$23,'S8'!$B$6:$B$23,$A54,'S8'!$E$6:$E$23,"Ambos")+SUMIFS('S9'!$I$6:$I$15,'S9'!$B$6:$B$15,$A54,'S9'!$E$6:$E$15,"Diego")+SUMIFS('S9'!$I$6:$I$15,'S9'!$B$6:$B$15,$A54,'S9'!$E$6:$E$15,"Ambos")+SUMIFS('S10'!$I$6:$I$13,'S10'!$B$6:$B$13,$A54,'S10'!$E$6:$E$13,"Diego")+SUMIFS('S10'!$I$6:$I$13,'S10'!$B$6:$B$13,$A54,'S10'!$E$6:$E$13,"Ambos")+SUMIFS('Holgura'!$I$6:$I$11,'Holgura'!$B$6:$B$11,$A54,'Holgura'!$E$6:$E$11,"Diego")+SUMIFS('Holgura'!$I$6:$I$11,'Holgura'!$B$6:$B$11,$A54,'Holgura'!$E$6:$E$11,"Ambos")+SUMIFS('Entrega'!$I$6:$I$9,'Entrega'!$B$6:$B$9,$A54,'Entrega'!$E$6:$E$9,"Diego")+SUMIFS('Entrega'!$I$6:$I$9,'Entrega'!$B$6:$B$9,$A54,'Entrega'!$E$6:$E$9,"Ambos")+SUMIFS('Defensa'!$I$6:$I$10,'Defensa'!$B$6:$B$10,$A54,'Defensa'!$E$6:$E$10,"Diego")+SUMIFS('Defensa'!$I$6:$I$10,'Defensa'!$B$6:$B$10,$A54,'Defensa'!$E$6:$E$10,"Ambos")</f>
         <v/>
       </c>
       <c r="F54" s="21">
-        <f>COUNTIFS('S1'!$B$6:$B$32,$A54,'S1'!$E$6:$E$32,"Víctor")+COUNTIFS('S1'!$B$6:$B$32,$A54,'S1'!$E$6:$E$32,"Ambos")+COUNTIFS('S2'!$B$6:$B$23,$A54,'S2'!$E$6:$E$23,"Víctor")+COUNTIFS('S2'!$B$6:$B$23,$A54,'S2'!$E$6:$E$23,"Ambos")+COUNTIFS('S3'!$B$6:$B$19,$A54,'S3'!$E$6:$E$19,"Víctor")+COUNTIFS('S3'!$B$6:$B$19,$A54,'S3'!$E$6:$E$19,"Ambos")+COUNTIFS('S4'!$B$6:$B$20,$A54,'S4'!$E$6:$E$20,"Víctor")+COUNTIFS('S4'!$B$6:$B$20,$A54,'S4'!$E$6:$E$20,"Ambos")+COUNTIFS('S5'!$B$6:$B$20,$A54,'S5'!$E$6:$E$20,"Víctor")+COUNTIFS('S5'!$B$6:$B$20,$A54,'S5'!$E$6:$E$20,"Ambos")+COUNTIFS('S6'!$B$6:$B$17,$A54,'S6'!$E$6:$E$17,"Víctor")+COUNTIFS('S6'!$B$6:$B$17,$A54,'S6'!$E$6:$E$17,"Ambos")+COUNTIFS('S7'!$B$6:$B$19,$A54,'S7'!$E$6:$E$19,"Víctor")+COUNTIFS('S7'!$B$6:$B$19,$A54,'S7'!$E$6:$E$19,"Ambos")+COUNTIFS('S8'!$B$6:$B$23,$A54,'S8'!$E$6:$E$23,"Víctor")+COUNTIFS('S8'!$B$6:$B$23,$A54,'S8'!$E$6:$E$23,"Ambos")+COUNTIFS('S9'!$B$6:$B$15,$A54,'S9'!$E$6:$E$15,"Víctor")+COUNTIFS('S9'!$B$6:$B$15,$A54,'S9'!$E$6:$E$15,"Ambos")+COUNTIFS('S10'!$B$6:$B$13,$A54,'S10'!$E$6:$E$13,"Víctor")+COUNTIFS('S10'!$B$6:$B$13,$A54,'S10'!$E$6:$E$13,"Ambos")+COUNTIFS('Holgura'!$B$6:$B$11,$A54,'Holgura'!$E$6:$E$11,"Víctor")+COUNTIFS('Holgura'!$B$6:$B$11,$A54,'Holgura'!$E$6:$E$11,"Ambos")+COUNTIFS('Entrega'!$B$6:$B$9,$A54,'Entrega'!$E$6:$E$9,"Víctor")+COUNTIFS('Entrega'!$B$6:$B$9,$A54,'Entrega'!$E$6:$E$9,"Ambos")+COUNTIFS('Defensa'!$B$6:$B$10,$A54,'Defensa'!$E$6:$E$10,"Víctor")+COUNTIFS('Defensa'!$B$6:$B$10,$A54,'Defensa'!$E$6:$E$10,"Ambos")</f>
+        <f>COUNTIFS('S1'!$B$6:$B$32,$A54,'S1'!$E$6:$E$32,"Víctor")+COUNTIFS('S1'!$B$6:$B$32,$A54,'S1'!$E$6:$E$32,"Ambos")+COUNTIFS('S2'!$B$6:$B$23,$A54,'S2'!$E$6:$E$23,"Víctor")+COUNTIFS('S2'!$B$6:$B$23,$A54,'S2'!$E$6:$E$23,"Ambos")+COUNTIFS('S3'!$B$6:$B$24,$A54,'S3'!$E$6:$E$24,"Víctor")+COUNTIFS('S3'!$B$6:$B$24,$A54,'S3'!$E$6:$E$24,"Ambos")+COUNTIFS('S4'!$B$6:$B$22,$A54,'S4'!$E$6:$E$22,"Víctor")+COUNTIFS('S4'!$B$6:$B$22,$A54,'S4'!$E$6:$E$22,"Ambos")+COUNTIFS('S5'!$B$6:$B$20,$A54,'S5'!$E$6:$E$20,"Víctor")+COUNTIFS('S5'!$B$6:$B$20,$A54,'S5'!$E$6:$E$20,"Ambos")+COUNTIFS('S6'!$B$6:$B$17,$A54,'S6'!$E$6:$E$17,"Víctor")+COUNTIFS('S6'!$B$6:$B$17,$A54,'S6'!$E$6:$E$17,"Ambos")+COUNTIFS('S7'!$B$6:$B$19,$A54,'S7'!$E$6:$E$19,"Víctor")+COUNTIFS('S7'!$B$6:$B$19,$A54,'S7'!$E$6:$E$19,"Ambos")+COUNTIFS('S8'!$B$6:$B$23,$A54,'S8'!$E$6:$E$23,"Víctor")+COUNTIFS('S8'!$B$6:$B$23,$A54,'S8'!$E$6:$E$23,"Ambos")+COUNTIFS('S9'!$B$6:$B$15,$A54,'S9'!$E$6:$E$15,"Víctor")+COUNTIFS('S9'!$B$6:$B$15,$A54,'S9'!$E$6:$E$15,"Ambos")+COUNTIFS('S10'!$B$6:$B$13,$A54,'S10'!$E$6:$E$13,"Víctor")+COUNTIFS('S10'!$B$6:$B$13,$A54,'S10'!$E$6:$E$13,"Ambos")+COUNTIFS('Holgura'!$B$6:$B$11,$A54,'Holgura'!$E$6:$E$11,"Víctor")+COUNTIFS('Holgura'!$B$6:$B$11,$A54,'Holgura'!$E$6:$E$11,"Ambos")+COUNTIFS('Entrega'!$B$6:$B$9,$A54,'Entrega'!$E$6:$E$9,"Víctor")+COUNTIFS('Entrega'!$B$6:$B$9,$A54,'Entrega'!$E$6:$E$9,"Ambos")+COUNTIFS('Defensa'!$B$6:$B$10,$A54,'Defensa'!$E$6:$E$10,"Víctor")+COUNTIFS('Defensa'!$B$6:$B$10,$A54,'Defensa'!$E$6:$E$10,"Ambos")</f>
         <v/>
       </c>
       <c r="G54" s="21">
-        <f>COUNTIFS('S1'!$B$6:$B$32,$A54,'S1'!$E$6:$E$32,"Diego")+COUNTIFS('S1'!$B$6:$B$32,$A54,'S1'!$E$6:$E$32,"Ambos")+COUNTIFS('S2'!$B$6:$B$23,$A54,'S2'!$E$6:$E$23,"Diego")+COUNTIFS('S2'!$B$6:$B$23,$A54,'S2'!$E$6:$E$23,"Ambos")+COUNTIFS('S3'!$B$6:$B$19,$A54,'S3'!$E$6:$E$19,"Diego")+COUNTIFS('S3'!$B$6:$B$19,$A54,'S3'!$E$6:$E$19,"Ambos")+COUNTIFS('S4'!$B$6:$B$20,$A54,'S4'!$E$6:$E$20,"Diego")+COUNTIFS('S4'!$B$6:$B$20,$A54,'S4'!$E$6:$E$20,"Ambos")+COUNTIFS('S5'!$B$6:$B$20,$A54,'S5'!$E$6:$E$20,"Diego")+COUNTIFS('S5'!$B$6:$B$20,$A54,'S5'!$E$6:$E$20,"Ambos")+COUNTIFS('S6'!$B$6:$B$17,$A54,'S6'!$E$6:$E$17,"Diego")+COUNTIFS('S6'!$B$6:$B$17,$A54,'S6'!$E$6:$E$17,"Ambos")+COUNTIFS('S7'!$B$6:$B$19,$A54,'S7'!$E$6:$E$19,"Diego")+COUNTIFS('S7'!$B$6:$B$19,$A54,'S7'!$E$6:$E$19,"Ambos")+COUNTIFS('S8'!$B$6:$B$23,$A54,'S8'!$E$6:$E$23,"Diego")+COUNTIFS('S8'!$B$6:$B$23,$A54,'S8'!$E$6:$E$23,"Ambos")+COUNTIFS('S9'!$B$6:$B$15,$A54,'S9'!$E$6:$E$15,"Diego")+COUNTIFS('S9'!$B$6:$B$15,$A54,'S9'!$E$6:$E$15,"Ambos")+COUNTIFS('S10'!$B$6:$B$13,$A54,'S10'!$E$6:$E$13,"Diego")+COUNTIFS('S10'!$B$6:$B$13,$A54,'S10'!$E$6:$E$13,"Ambos")+COUNTIFS('Holgura'!$B$6:$B$11,$A54,'Holgura'!$E$6:$E$11,"Diego")+COUNTIFS('Holgura'!$B$6:$B$11,$A54,'Holgura'!$E$6:$E$11,"Ambos")+COUNTIFS('Entrega'!$B$6:$B$9,$A54,'Entrega'!$E$6:$E$9,"Diego")+COUNTIFS('Entrega'!$B$6:$B$9,$A54,'Entrega'!$E$6:$E$9,"Ambos")+COUNTIFS('Defensa'!$B$6:$B$10,$A54,'Defensa'!$E$6:$E$10,"Diego")+COUNTIFS('Defensa'!$B$6:$B$10,$A54,'Defensa'!$E$6:$E$10,"Ambos")</f>
+        <f>COUNTIFS('S1'!$B$6:$B$32,$A54,'S1'!$E$6:$E$32,"Diego")+COUNTIFS('S1'!$B$6:$B$32,$A54,'S1'!$E$6:$E$32,"Ambos")+COUNTIFS('S2'!$B$6:$B$23,$A54,'S2'!$E$6:$E$23,"Diego")+COUNTIFS('S2'!$B$6:$B$23,$A54,'S2'!$E$6:$E$23,"Ambos")+COUNTIFS('S3'!$B$6:$B$24,$A54,'S3'!$E$6:$E$24,"Diego")+COUNTIFS('S3'!$B$6:$B$24,$A54,'S3'!$E$6:$E$24,"Ambos")+COUNTIFS('S4'!$B$6:$B$22,$A54,'S4'!$E$6:$E$22,"Diego")+COUNTIFS('S4'!$B$6:$B$22,$A54,'S4'!$E$6:$E$22,"Ambos")+COUNTIFS('S5'!$B$6:$B$20,$A54,'S5'!$E$6:$E$20,"Diego")+COUNTIFS('S5'!$B$6:$B$20,$A54,'S5'!$E$6:$E$20,"Ambos")+COUNTIFS('S6'!$B$6:$B$17,$A54,'S6'!$E$6:$E$17,"Diego")+COUNTIFS('S6'!$B$6:$B$17,$A54,'S6'!$E$6:$E$17,"Ambos")+COUNTIFS('S7'!$B$6:$B$19,$A54,'S7'!$E$6:$E$19,"Diego")+COUNTIFS('S7'!$B$6:$B$19,$A54,'S7'!$E$6:$E$19,"Ambos")+COUNTIFS('S8'!$B$6:$B$23,$A54,'S8'!$E$6:$E$23,"Diego")+COUNTIFS('S8'!$B$6:$B$23,$A54,'S8'!$E$6:$E$23,"Ambos")+COUNTIFS('S9'!$B$6:$B$15,$A54,'S9'!$E$6:$E$15,"Diego")+COUNTIFS('S9'!$B$6:$B$15,$A54,'S9'!$E$6:$E$15,"Ambos")+COUNTIFS('S10'!$B$6:$B$13,$A54,'S10'!$E$6:$E$13,"Diego")+COUNTIFS('S10'!$B$6:$B$13,$A54,'S10'!$E$6:$E$13,"Ambos")+COUNTIFS('Holgura'!$B$6:$B$11,$A54,'Holgura'!$E$6:$E$11,"Diego")+COUNTIFS('Holgura'!$B$6:$B$11,$A54,'Holgura'!$E$6:$E$11,"Ambos")+COUNTIFS('Entrega'!$B$6:$B$9,$A54,'Entrega'!$E$6:$E$9,"Diego")+COUNTIFS('Entrega'!$B$6:$B$9,$A54,'Entrega'!$E$6:$E$9,"Ambos")+COUNTIFS('Defensa'!$B$6:$B$10,$A54,'Defensa'!$E$6:$E$10,"Diego")+COUNTIFS('Defensa'!$B$6:$B$10,$A54,'Defensa'!$E$6:$E$10,"Ambos")</f>
         <v/>
       </c>
     </row>
@@ -10130,19 +10151,19 @@
         <v/>
       </c>
       <c r="D55" s="21">
-        <f>SUMIFS('S1'!$I$6:$I$32,'S1'!$B$6:$B$32,$A55,'S1'!$E$6:$E$32,"Víctor")+SUMIFS('S1'!$I$6:$I$32,'S1'!$B$6:$B$32,$A55,'S1'!$E$6:$E$32,"Ambos")+SUMIFS('S2'!$I$6:$I$23,'S2'!$B$6:$B$23,$A55,'S2'!$E$6:$E$23,"Víctor")+SUMIFS('S2'!$I$6:$I$23,'S2'!$B$6:$B$23,$A55,'S2'!$E$6:$E$23,"Ambos")+SUMIFS('S3'!$I$6:$I$19,'S3'!$B$6:$B$19,$A55,'S3'!$E$6:$E$19,"Víctor")+SUMIFS('S3'!$I$6:$I$19,'S3'!$B$6:$B$19,$A55,'S3'!$E$6:$E$19,"Ambos")+SUMIFS('S4'!$I$6:$I$20,'S4'!$B$6:$B$20,$A55,'S4'!$E$6:$E$20,"Víctor")+SUMIFS('S4'!$I$6:$I$20,'S4'!$B$6:$B$20,$A55,'S4'!$E$6:$E$20,"Ambos")+SUMIFS('S5'!$I$6:$I$20,'S5'!$B$6:$B$20,$A55,'S5'!$E$6:$E$20,"Víctor")+SUMIFS('S5'!$I$6:$I$20,'S5'!$B$6:$B$20,$A55,'S5'!$E$6:$E$20,"Ambos")+SUMIFS('S6'!$I$6:$I$17,'S6'!$B$6:$B$17,$A55,'S6'!$E$6:$E$17,"Víctor")+SUMIFS('S6'!$I$6:$I$17,'S6'!$B$6:$B$17,$A55,'S6'!$E$6:$E$17,"Ambos")+SUMIFS('S7'!$I$6:$I$19,'S7'!$B$6:$B$19,$A55,'S7'!$E$6:$E$19,"Víctor")+SUMIFS('S7'!$I$6:$I$19,'S7'!$B$6:$B$19,$A55,'S7'!$E$6:$E$19,"Ambos")+SUMIFS('S8'!$I$6:$I$23,'S8'!$B$6:$B$23,$A55,'S8'!$E$6:$E$23,"Víctor")+SUMIFS('S8'!$I$6:$I$23,'S8'!$B$6:$B$23,$A55,'S8'!$E$6:$E$23,"Ambos")+SUMIFS('S9'!$I$6:$I$15,'S9'!$B$6:$B$15,$A55,'S9'!$E$6:$E$15,"Víctor")+SUMIFS('S9'!$I$6:$I$15,'S9'!$B$6:$B$15,$A55,'S9'!$E$6:$E$15,"Ambos")+SUMIFS('S10'!$I$6:$I$13,'S10'!$B$6:$B$13,$A55,'S10'!$E$6:$E$13,"Víctor")+SUMIFS('S10'!$I$6:$I$13,'S10'!$B$6:$B$13,$A55,'S10'!$E$6:$E$13,"Ambos")+SUMIFS('Holgura'!$I$6:$I$11,'Holgura'!$B$6:$B$11,$A55,'Holgura'!$E$6:$E$11,"Víctor")+SUMIFS('Holgura'!$I$6:$I$11,'Holgura'!$B$6:$B$11,$A55,'Holgura'!$E$6:$E$11,"Ambos")+SUMIFS('Entrega'!$I$6:$I$9,'Entrega'!$B$6:$B$9,$A55,'Entrega'!$E$6:$E$9,"Víctor")+SUMIFS('Entrega'!$I$6:$I$9,'Entrega'!$B$6:$B$9,$A55,'Entrega'!$E$6:$E$9,"Ambos")+SUMIFS('Defensa'!$I$6:$I$10,'Defensa'!$B$6:$B$10,$A55,'Defensa'!$E$6:$E$10,"Víctor")+SUMIFS('Defensa'!$I$6:$I$10,'Defensa'!$B$6:$B$10,$A55,'Defensa'!$E$6:$E$10,"Ambos")</f>
+        <f>SUMIFS('S1'!$I$6:$I$32,'S1'!$B$6:$B$32,$A55,'S1'!$E$6:$E$32,"Víctor")+SUMIFS('S1'!$I$6:$I$32,'S1'!$B$6:$B$32,$A55,'S1'!$E$6:$E$32,"Ambos")+SUMIFS('S2'!$I$6:$I$23,'S2'!$B$6:$B$23,$A55,'S2'!$E$6:$E$23,"Víctor")+SUMIFS('S2'!$I$6:$I$23,'S2'!$B$6:$B$23,$A55,'S2'!$E$6:$E$23,"Ambos")+SUMIFS('S3'!$I$6:$I$24,'S3'!$B$6:$B$24,$A55,'S3'!$E$6:$E$24,"Víctor")+SUMIFS('S3'!$I$6:$I$24,'S3'!$B$6:$B$24,$A55,'S3'!$E$6:$E$24,"Ambos")+SUMIFS('S4'!$I$6:$I$22,'S4'!$B$6:$B$22,$A55,'S4'!$E$6:$E$22,"Víctor")+SUMIFS('S4'!$I$6:$I$22,'S4'!$B$6:$B$22,$A55,'S4'!$E$6:$E$22,"Ambos")+SUMIFS('S5'!$I$6:$I$20,'S5'!$B$6:$B$20,$A55,'S5'!$E$6:$E$20,"Víctor")+SUMIFS('S5'!$I$6:$I$20,'S5'!$B$6:$B$20,$A55,'S5'!$E$6:$E$20,"Ambos")+SUMIFS('S6'!$I$6:$I$17,'S6'!$B$6:$B$17,$A55,'S6'!$E$6:$E$17,"Víctor")+SUMIFS('S6'!$I$6:$I$17,'S6'!$B$6:$B$17,$A55,'S6'!$E$6:$E$17,"Ambos")+SUMIFS('S7'!$I$6:$I$19,'S7'!$B$6:$B$19,$A55,'S7'!$E$6:$E$19,"Víctor")+SUMIFS('S7'!$I$6:$I$19,'S7'!$B$6:$B$19,$A55,'S7'!$E$6:$E$19,"Ambos")+SUMIFS('S8'!$I$6:$I$23,'S8'!$B$6:$B$23,$A55,'S8'!$E$6:$E$23,"Víctor")+SUMIFS('S8'!$I$6:$I$23,'S8'!$B$6:$B$23,$A55,'S8'!$E$6:$E$23,"Ambos")+SUMIFS('S9'!$I$6:$I$15,'S9'!$B$6:$B$15,$A55,'S9'!$E$6:$E$15,"Víctor")+SUMIFS('S9'!$I$6:$I$15,'S9'!$B$6:$B$15,$A55,'S9'!$E$6:$E$15,"Ambos")+SUMIFS('S10'!$I$6:$I$13,'S10'!$B$6:$B$13,$A55,'S10'!$E$6:$E$13,"Víctor")+SUMIFS('S10'!$I$6:$I$13,'S10'!$B$6:$B$13,$A55,'S10'!$E$6:$E$13,"Ambos")+SUMIFS('Holgura'!$I$6:$I$11,'Holgura'!$B$6:$B$11,$A55,'Holgura'!$E$6:$E$11,"Víctor")+SUMIFS('Holgura'!$I$6:$I$11,'Holgura'!$B$6:$B$11,$A55,'Holgura'!$E$6:$E$11,"Ambos")+SUMIFS('Entrega'!$I$6:$I$9,'Entrega'!$B$6:$B$9,$A55,'Entrega'!$E$6:$E$9,"Víctor")+SUMIFS('Entrega'!$I$6:$I$9,'Entrega'!$B$6:$B$9,$A55,'Entrega'!$E$6:$E$9,"Ambos")+SUMIFS('Defensa'!$I$6:$I$10,'Defensa'!$B$6:$B$10,$A55,'Defensa'!$E$6:$E$10,"Víctor")+SUMIFS('Defensa'!$I$6:$I$10,'Defensa'!$B$6:$B$10,$A55,'Defensa'!$E$6:$E$10,"Ambos")</f>
         <v/>
       </c>
       <c r="E55" s="21">
-        <f>SUMIFS('S1'!$I$6:$I$32,'S1'!$B$6:$B$32,$A55,'S1'!$E$6:$E$32,"Diego")+SUMIFS('S1'!$I$6:$I$32,'S1'!$B$6:$B$32,$A55,'S1'!$E$6:$E$32,"Ambos")+SUMIFS('S2'!$I$6:$I$23,'S2'!$B$6:$B$23,$A55,'S2'!$E$6:$E$23,"Diego")+SUMIFS('S2'!$I$6:$I$23,'S2'!$B$6:$B$23,$A55,'S2'!$E$6:$E$23,"Ambos")+SUMIFS('S3'!$I$6:$I$19,'S3'!$B$6:$B$19,$A55,'S3'!$E$6:$E$19,"Diego")+SUMIFS('S3'!$I$6:$I$19,'S3'!$B$6:$B$19,$A55,'S3'!$E$6:$E$19,"Ambos")+SUMIFS('S4'!$I$6:$I$20,'S4'!$B$6:$B$20,$A55,'S4'!$E$6:$E$20,"Diego")+SUMIFS('S4'!$I$6:$I$20,'S4'!$B$6:$B$20,$A55,'S4'!$E$6:$E$20,"Ambos")+SUMIFS('S5'!$I$6:$I$20,'S5'!$B$6:$B$20,$A55,'S5'!$E$6:$E$20,"Diego")+SUMIFS('S5'!$I$6:$I$20,'S5'!$B$6:$B$20,$A55,'S5'!$E$6:$E$20,"Ambos")+SUMIFS('S6'!$I$6:$I$17,'S6'!$B$6:$B$17,$A55,'S6'!$E$6:$E$17,"Diego")+SUMIFS('S6'!$I$6:$I$17,'S6'!$B$6:$B$17,$A55,'S6'!$E$6:$E$17,"Ambos")+SUMIFS('S7'!$I$6:$I$19,'S7'!$B$6:$B$19,$A55,'S7'!$E$6:$E$19,"Diego")+SUMIFS('S7'!$I$6:$I$19,'S7'!$B$6:$B$19,$A55,'S7'!$E$6:$E$19,"Ambos")+SUMIFS('S8'!$I$6:$I$23,'S8'!$B$6:$B$23,$A55,'S8'!$E$6:$E$23,"Diego")+SUMIFS('S8'!$I$6:$I$23,'S8'!$B$6:$B$23,$A55,'S8'!$E$6:$E$23,"Ambos")+SUMIFS('S9'!$I$6:$I$15,'S9'!$B$6:$B$15,$A55,'S9'!$E$6:$E$15,"Diego")+SUMIFS('S9'!$I$6:$I$15,'S9'!$B$6:$B$15,$A55,'S9'!$E$6:$E$15,"Ambos")+SUMIFS('S10'!$I$6:$I$13,'S10'!$B$6:$B$13,$A55,'S10'!$E$6:$E$13,"Diego")+SUMIFS('S10'!$I$6:$I$13,'S10'!$B$6:$B$13,$A55,'S10'!$E$6:$E$13,"Ambos")+SUMIFS('Holgura'!$I$6:$I$11,'Holgura'!$B$6:$B$11,$A55,'Holgura'!$E$6:$E$11,"Diego")+SUMIFS('Holgura'!$I$6:$I$11,'Holgura'!$B$6:$B$11,$A55,'Holgura'!$E$6:$E$11,"Ambos")+SUMIFS('Entrega'!$I$6:$I$9,'Entrega'!$B$6:$B$9,$A55,'Entrega'!$E$6:$E$9,"Diego")+SUMIFS('Entrega'!$I$6:$I$9,'Entrega'!$B$6:$B$9,$A55,'Entrega'!$E$6:$E$9,"Ambos")+SUMIFS('Defensa'!$I$6:$I$10,'Defensa'!$B$6:$B$10,$A55,'Defensa'!$E$6:$E$10,"Diego")+SUMIFS('Defensa'!$I$6:$I$10,'Defensa'!$B$6:$B$10,$A55,'Defensa'!$E$6:$E$10,"Ambos")</f>
+        <f>SUMIFS('S1'!$I$6:$I$32,'S1'!$B$6:$B$32,$A55,'S1'!$E$6:$E$32,"Diego")+SUMIFS('S1'!$I$6:$I$32,'S1'!$B$6:$B$32,$A55,'S1'!$E$6:$E$32,"Ambos")+SUMIFS('S2'!$I$6:$I$23,'S2'!$B$6:$B$23,$A55,'S2'!$E$6:$E$23,"Diego")+SUMIFS('S2'!$I$6:$I$23,'S2'!$B$6:$B$23,$A55,'S2'!$E$6:$E$23,"Ambos")+SUMIFS('S3'!$I$6:$I$24,'S3'!$B$6:$B$24,$A55,'S3'!$E$6:$E$24,"Diego")+SUMIFS('S3'!$I$6:$I$24,'S3'!$B$6:$B$24,$A55,'S3'!$E$6:$E$24,"Ambos")+SUMIFS('S4'!$I$6:$I$22,'S4'!$B$6:$B$22,$A55,'S4'!$E$6:$E$22,"Diego")+SUMIFS('S4'!$I$6:$I$22,'S4'!$B$6:$B$22,$A55,'S4'!$E$6:$E$22,"Ambos")+SUMIFS('S5'!$I$6:$I$20,'S5'!$B$6:$B$20,$A55,'S5'!$E$6:$E$20,"Diego")+SUMIFS('S5'!$I$6:$I$20,'S5'!$B$6:$B$20,$A55,'S5'!$E$6:$E$20,"Ambos")+SUMIFS('S6'!$I$6:$I$17,'S6'!$B$6:$B$17,$A55,'S6'!$E$6:$E$17,"Diego")+SUMIFS('S6'!$I$6:$I$17,'S6'!$B$6:$B$17,$A55,'S6'!$E$6:$E$17,"Ambos")+SUMIFS('S7'!$I$6:$I$19,'S7'!$B$6:$B$19,$A55,'S7'!$E$6:$E$19,"Diego")+SUMIFS('S7'!$I$6:$I$19,'S7'!$B$6:$B$19,$A55,'S7'!$E$6:$E$19,"Ambos")+SUMIFS('S8'!$I$6:$I$23,'S8'!$B$6:$B$23,$A55,'S8'!$E$6:$E$23,"Diego")+SUMIFS('S8'!$I$6:$I$23,'S8'!$B$6:$B$23,$A55,'S8'!$E$6:$E$23,"Ambos")+SUMIFS('S9'!$I$6:$I$15,'S9'!$B$6:$B$15,$A55,'S9'!$E$6:$E$15,"Diego")+SUMIFS('S9'!$I$6:$I$15,'S9'!$B$6:$B$15,$A55,'S9'!$E$6:$E$15,"Ambos")+SUMIFS('S10'!$I$6:$I$13,'S10'!$B$6:$B$13,$A55,'S10'!$E$6:$E$13,"Diego")+SUMIFS('S10'!$I$6:$I$13,'S10'!$B$6:$B$13,$A55,'S10'!$E$6:$E$13,"Ambos")+SUMIFS('Holgura'!$I$6:$I$11,'Holgura'!$B$6:$B$11,$A55,'Holgura'!$E$6:$E$11,"Diego")+SUMIFS('Holgura'!$I$6:$I$11,'Holgura'!$B$6:$B$11,$A55,'Holgura'!$E$6:$E$11,"Ambos")+SUMIFS('Entrega'!$I$6:$I$9,'Entrega'!$B$6:$B$9,$A55,'Entrega'!$E$6:$E$9,"Diego")+SUMIFS('Entrega'!$I$6:$I$9,'Entrega'!$B$6:$B$9,$A55,'Entrega'!$E$6:$E$9,"Ambos")+SUMIFS('Defensa'!$I$6:$I$10,'Defensa'!$B$6:$B$10,$A55,'Defensa'!$E$6:$E$10,"Diego")+SUMIFS('Defensa'!$I$6:$I$10,'Defensa'!$B$6:$B$10,$A55,'Defensa'!$E$6:$E$10,"Ambos")</f>
         <v/>
       </c>
       <c r="F55" s="21">
-        <f>COUNTIFS('S1'!$B$6:$B$32,$A55,'S1'!$E$6:$E$32,"Víctor")+COUNTIFS('S1'!$B$6:$B$32,$A55,'S1'!$E$6:$E$32,"Ambos")+COUNTIFS('S2'!$B$6:$B$23,$A55,'S2'!$E$6:$E$23,"Víctor")+COUNTIFS('S2'!$B$6:$B$23,$A55,'S2'!$E$6:$E$23,"Ambos")+COUNTIFS('S3'!$B$6:$B$19,$A55,'S3'!$E$6:$E$19,"Víctor")+COUNTIFS('S3'!$B$6:$B$19,$A55,'S3'!$E$6:$E$19,"Ambos")+COUNTIFS('S4'!$B$6:$B$20,$A55,'S4'!$E$6:$E$20,"Víctor")+COUNTIFS('S4'!$B$6:$B$20,$A55,'S4'!$E$6:$E$20,"Ambos")+COUNTIFS('S5'!$B$6:$B$20,$A55,'S5'!$E$6:$E$20,"Víctor")+COUNTIFS('S5'!$B$6:$B$20,$A55,'S5'!$E$6:$E$20,"Ambos")+COUNTIFS('S6'!$B$6:$B$17,$A55,'S6'!$E$6:$E$17,"Víctor")+COUNTIFS('S6'!$B$6:$B$17,$A55,'S6'!$E$6:$E$17,"Ambos")+COUNTIFS('S7'!$B$6:$B$19,$A55,'S7'!$E$6:$E$19,"Víctor")+COUNTIFS('S7'!$B$6:$B$19,$A55,'S7'!$E$6:$E$19,"Ambos")+COUNTIFS('S8'!$B$6:$B$23,$A55,'S8'!$E$6:$E$23,"Víctor")+COUNTIFS('S8'!$B$6:$B$23,$A55,'S8'!$E$6:$E$23,"Ambos")+COUNTIFS('S9'!$B$6:$B$15,$A55,'S9'!$E$6:$E$15,"Víctor")+COUNTIFS('S9'!$B$6:$B$15,$A55,'S9'!$E$6:$E$15,"Ambos")+COUNTIFS('S10'!$B$6:$B$13,$A55,'S10'!$E$6:$E$13,"Víctor")+COUNTIFS('S10'!$B$6:$B$13,$A55,'S10'!$E$6:$E$13,"Ambos")+COUNTIFS('Holgura'!$B$6:$B$11,$A55,'Holgura'!$E$6:$E$11,"Víctor")+COUNTIFS('Holgura'!$B$6:$B$11,$A55,'Holgura'!$E$6:$E$11,"Ambos")+COUNTIFS('Entrega'!$B$6:$B$9,$A55,'Entrega'!$E$6:$E$9,"Víctor")+COUNTIFS('Entrega'!$B$6:$B$9,$A55,'Entrega'!$E$6:$E$9,"Ambos")+COUNTIFS('Defensa'!$B$6:$B$10,$A55,'Defensa'!$E$6:$E$10,"Víctor")+COUNTIFS('Defensa'!$B$6:$B$10,$A55,'Defensa'!$E$6:$E$10,"Ambos")</f>
+        <f>COUNTIFS('S1'!$B$6:$B$32,$A55,'S1'!$E$6:$E$32,"Víctor")+COUNTIFS('S1'!$B$6:$B$32,$A55,'S1'!$E$6:$E$32,"Ambos")+COUNTIFS('S2'!$B$6:$B$23,$A55,'S2'!$E$6:$E$23,"Víctor")+COUNTIFS('S2'!$B$6:$B$23,$A55,'S2'!$E$6:$E$23,"Ambos")+COUNTIFS('S3'!$B$6:$B$24,$A55,'S3'!$E$6:$E$24,"Víctor")+COUNTIFS('S3'!$B$6:$B$24,$A55,'S3'!$E$6:$E$24,"Ambos")+COUNTIFS('S4'!$B$6:$B$22,$A55,'S4'!$E$6:$E$22,"Víctor")+COUNTIFS('S4'!$B$6:$B$22,$A55,'S4'!$E$6:$E$22,"Ambos")+COUNTIFS('S5'!$B$6:$B$20,$A55,'S5'!$E$6:$E$20,"Víctor")+COUNTIFS('S5'!$B$6:$B$20,$A55,'S5'!$E$6:$E$20,"Ambos")+COUNTIFS('S6'!$B$6:$B$17,$A55,'S6'!$E$6:$E$17,"Víctor")+COUNTIFS('S6'!$B$6:$B$17,$A55,'S6'!$E$6:$E$17,"Ambos")+COUNTIFS('S7'!$B$6:$B$19,$A55,'S7'!$E$6:$E$19,"Víctor")+COUNTIFS('S7'!$B$6:$B$19,$A55,'S7'!$E$6:$E$19,"Ambos")+COUNTIFS('S8'!$B$6:$B$23,$A55,'S8'!$E$6:$E$23,"Víctor")+COUNTIFS('S8'!$B$6:$B$23,$A55,'S8'!$E$6:$E$23,"Ambos")+COUNTIFS('S9'!$B$6:$B$15,$A55,'S9'!$E$6:$E$15,"Víctor")+COUNTIFS('S9'!$B$6:$B$15,$A55,'S9'!$E$6:$E$15,"Ambos")+COUNTIFS('S10'!$B$6:$B$13,$A55,'S10'!$E$6:$E$13,"Víctor")+COUNTIFS('S10'!$B$6:$B$13,$A55,'S10'!$E$6:$E$13,"Ambos")+COUNTIFS('Holgura'!$B$6:$B$11,$A55,'Holgura'!$E$6:$E$11,"Víctor")+COUNTIFS('Holgura'!$B$6:$B$11,$A55,'Holgura'!$E$6:$E$11,"Ambos")+COUNTIFS('Entrega'!$B$6:$B$9,$A55,'Entrega'!$E$6:$E$9,"Víctor")+COUNTIFS('Entrega'!$B$6:$B$9,$A55,'Entrega'!$E$6:$E$9,"Ambos")+COUNTIFS('Defensa'!$B$6:$B$10,$A55,'Defensa'!$E$6:$E$10,"Víctor")+COUNTIFS('Defensa'!$B$6:$B$10,$A55,'Defensa'!$E$6:$E$10,"Ambos")</f>
         <v/>
       </c>
       <c r="G55" s="21">
-        <f>COUNTIFS('S1'!$B$6:$B$32,$A55,'S1'!$E$6:$E$32,"Diego")+COUNTIFS('S1'!$B$6:$B$32,$A55,'S1'!$E$6:$E$32,"Ambos")+COUNTIFS('S2'!$B$6:$B$23,$A55,'S2'!$E$6:$E$23,"Diego")+COUNTIFS('S2'!$B$6:$B$23,$A55,'S2'!$E$6:$E$23,"Ambos")+COUNTIFS('S3'!$B$6:$B$19,$A55,'S3'!$E$6:$E$19,"Diego")+COUNTIFS('S3'!$B$6:$B$19,$A55,'S3'!$E$6:$E$19,"Ambos")+COUNTIFS('S4'!$B$6:$B$20,$A55,'S4'!$E$6:$E$20,"Diego")+COUNTIFS('S4'!$B$6:$B$20,$A55,'S4'!$E$6:$E$20,"Ambos")+COUNTIFS('S5'!$B$6:$B$20,$A55,'S5'!$E$6:$E$20,"Diego")+COUNTIFS('S5'!$B$6:$B$20,$A55,'S5'!$E$6:$E$20,"Ambos")+COUNTIFS('S6'!$B$6:$B$17,$A55,'S6'!$E$6:$E$17,"Diego")+COUNTIFS('S6'!$B$6:$B$17,$A55,'S6'!$E$6:$E$17,"Ambos")+COUNTIFS('S7'!$B$6:$B$19,$A55,'S7'!$E$6:$E$19,"Diego")+COUNTIFS('S7'!$B$6:$B$19,$A55,'S7'!$E$6:$E$19,"Ambos")+COUNTIFS('S8'!$B$6:$B$23,$A55,'S8'!$E$6:$E$23,"Diego")+COUNTIFS('S8'!$B$6:$B$23,$A55,'S8'!$E$6:$E$23,"Ambos")+COUNTIFS('S9'!$B$6:$B$15,$A55,'S9'!$E$6:$E$15,"Diego")+COUNTIFS('S9'!$B$6:$B$15,$A55,'S9'!$E$6:$E$15,"Ambos")+COUNTIFS('S10'!$B$6:$B$13,$A55,'S10'!$E$6:$E$13,"Diego")+COUNTIFS('S10'!$B$6:$B$13,$A55,'S10'!$E$6:$E$13,"Ambos")+COUNTIFS('Holgura'!$B$6:$B$11,$A55,'Holgura'!$E$6:$E$11,"Diego")+COUNTIFS('Holgura'!$B$6:$B$11,$A55,'Holgura'!$E$6:$E$11,"Ambos")+COUNTIFS('Entrega'!$B$6:$B$9,$A55,'Entrega'!$E$6:$E$9,"Diego")+COUNTIFS('Entrega'!$B$6:$B$9,$A55,'Entrega'!$E$6:$E$9,"Ambos")+COUNTIFS('Defensa'!$B$6:$B$10,$A55,'Defensa'!$E$6:$E$10,"Diego")+COUNTIFS('Defensa'!$B$6:$B$10,$A55,'Defensa'!$E$6:$E$10,"Ambos")</f>
+        <f>COUNTIFS('S1'!$B$6:$B$32,$A55,'S1'!$E$6:$E$32,"Diego")+COUNTIFS('S1'!$B$6:$B$32,$A55,'S1'!$E$6:$E$32,"Ambos")+COUNTIFS('S2'!$B$6:$B$23,$A55,'S2'!$E$6:$E$23,"Diego")+COUNTIFS('S2'!$B$6:$B$23,$A55,'S2'!$E$6:$E$23,"Ambos")+COUNTIFS('S3'!$B$6:$B$24,$A55,'S3'!$E$6:$E$24,"Diego")+COUNTIFS('S3'!$B$6:$B$24,$A55,'S3'!$E$6:$E$24,"Ambos")+COUNTIFS('S4'!$B$6:$B$22,$A55,'S4'!$E$6:$E$22,"Diego")+COUNTIFS('S4'!$B$6:$B$22,$A55,'S4'!$E$6:$E$22,"Ambos")+COUNTIFS('S5'!$B$6:$B$20,$A55,'S5'!$E$6:$E$20,"Diego")+COUNTIFS('S5'!$B$6:$B$20,$A55,'S5'!$E$6:$E$20,"Ambos")+COUNTIFS('S6'!$B$6:$B$17,$A55,'S6'!$E$6:$E$17,"Diego")+COUNTIFS('S6'!$B$6:$B$17,$A55,'S6'!$E$6:$E$17,"Ambos")+COUNTIFS('S7'!$B$6:$B$19,$A55,'S7'!$E$6:$E$19,"Diego")+COUNTIFS('S7'!$B$6:$B$19,$A55,'S7'!$E$6:$E$19,"Ambos")+COUNTIFS('S8'!$B$6:$B$23,$A55,'S8'!$E$6:$E$23,"Diego")+COUNTIFS('S8'!$B$6:$B$23,$A55,'S8'!$E$6:$E$23,"Ambos")+COUNTIFS('S9'!$B$6:$B$15,$A55,'S9'!$E$6:$E$15,"Diego")+COUNTIFS('S9'!$B$6:$B$15,$A55,'S9'!$E$6:$E$15,"Ambos")+COUNTIFS('S10'!$B$6:$B$13,$A55,'S10'!$E$6:$E$13,"Diego")+COUNTIFS('S10'!$B$6:$B$13,$A55,'S10'!$E$6:$E$13,"Ambos")+COUNTIFS('Holgura'!$B$6:$B$11,$A55,'Holgura'!$E$6:$E$11,"Diego")+COUNTIFS('Holgura'!$B$6:$B$11,$A55,'Holgura'!$E$6:$E$11,"Ambos")+COUNTIFS('Entrega'!$B$6:$B$9,$A55,'Entrega'!$E$6:$E$9,"Diego")+COUNTIFS('Entrega'!$B$6:$B$9,$A55,'Entrega'!$E$6:$E$9,"Ambos")+COUNTIFS('Defensa'!$B$6:$B$10,$A55,'Defensa'!$E$6:$E$10,"Diego")+COUNTIFS('Defensa'!$B$6:$B$10,$A55,'Defensa'!$E$6:$E$10,"Ambos")</f>
         <v/>
       </c>
     </row>
@@ -10159,19 +10180,19 @@
         <v/>
       </c>
       <c r="D56" s="21">
-        <f>SUMIFS('S1'!$I$6:$I$32,'S1'!$B$6:$B$32,$A56,'S1'!$E$6:$E$32,"Víctor")+SUMIFS('S1'!$I$6:$I$32,'S1'!$B$6:$B$32,$A56,'S1'!$E$6:$E$32,"Ambos")+SUMIFS('S2'!$I$6:$I$23,'S2'!$B$6:$B$23,$A56,'S2'!$E$6:$E$23,"Víctor")+SUMIFS('S2'!$I$6:$I$23,'S2'!$B$6:$B$23,$A56,'S2'!$E$6:$E$23,"Ambos")+SUMIFS('S3'!$I$6:$I$19,'S3'!$B$6:$B$19,$A56,'S3'!$E$6:$E$19,"Víctor")+SUMIFS('S3'!$I$6:$I$19,'S3'!$B$6:$B$19,$A56,'S3'!$E$6:$E$19,"Ambos")+SUMIFS('S4'!$I$6:$I$20,'S4'!$B$6:$B$20,$A56,'S4'!$E$6:$E$20,"Víctor")+SUMIFS('S4'!$I$6:$I$20,'S4'!$B$6:$B$20,$A56,'S4'!$E$6:$E$20,"Ambos")+SUMIFS('S5'!$I$6:$I$20,'S5'!$B$6:$B$20,$A56,'S5'!$E$6:$E$20,"Víctor")+SUMIFS('S5'!$I$6:$I$20,'S5'!$B$6:$B$20,$A56,'S5'!$E$6:$E$20,"Ambos")+SUMIFS('S6'!$I$6:$I$17,'S6'!$B$6:$B$17,$A56,'S6'!$E$6:$E$17,"Víctor")+SUMIFS('S6'!$I$6:$I$17,'S6'!$B$6:$B$17,$A56,'S6'!$E$6:$E$17,"Ambos")+SUMIFS('S7'!$I$6:$I$19,'S7'!$B$6:$B$19,$A56,'S7'!$E$6:$E$19,"Víctor")+SUMIFS('S7'!$I$6:$I$19,'S7'!$B$6:$B$19,$A56,'S7'!$E$6:$E$19,"Ambos")+SUMIFS('S8'!$I$6:$I$23,'S8'!$B$6:$B$23,$A56,'S8'!$E$6:$E$23,"Víctor")+SUMIFS('S8'!$I$6:$I$23,'S8'!$B$6:$B$23,$A56,'S8'!$E$6:$E$23,"Ambos")+SUMIFS('S9'!$I$6:$I$15,'S9'!$B$6:$B$15,$A56,'S9'!$E$6:$E$15,"Víctor")+SUMIFS('S9'!$I$6:$I$15,'S9'!$B$6:$B$15,$A56,'S9'!$E$6:$E$15,"Ambos")+SUMIFS('S10'!$I$6:$I$13,'S10'!$B$6:$B$13,$A56,'S10'!$E$6:$E$13,"Víctor")+SUMIFS('S10'!$I$6:$I$13,'S10'!$B$6:$B$13,$A56,'S10'!$E$6:$E$13,"Ambos")+SUMIFS('Holgura'!$I$6:$I$11,'Holgura'!$B$6:$B$11,$A56,'Holgura'!$E$6:$E$11,"Víctor")+SUMIFS('Holgura'!$I$6:$I$11,'Holgura'!$B$6:$B$11,$A56,'Holgura'!$E$6:$E$11,"Ambos")+SUMIFS('Entrega'!$I$6:$I$9,'Entrega'!$B$6:$B$9,$A56,'Entrega'!$E$6:$E$9,"Víctor")+SUMIFS('Entrega'!$I$6:$I$9,'Entrega'!$B$6:$B$9,$A56,'Entrega'!$E$6:$E$9,"Ambos")+SUMIFS('Defensa'!$I$6:$I$10,'Defensa'!$B$6:$B$10,$A56,'Defensa'!$E$6:$E$10,"Víctor")+SUMIFS('Defensa'!$I$6:$I$10,'Defensa'!$B$6:$B$10,$A56,'Defensa'!$E$6:$E$10,"Ambos")</f>
+        <f>SUMIFS('S1'!$I$6:$I$32,'S1'!$B$6:$B$32,$A56,'S1'!$E$6:$E$32,"Víctor")+SUMIFS('S1'!$I$6:$I$32,'S1'!$B$6:$B$32,$A56,'S1'!$E$6:$E$32,"Ambos")+SUMIFS('S2'!$I$6:$I$23,'S2'!$B$6:$B$23,$A56,'S2'!$E$6:$E$23,"Víctor")+SUMIFS('S2'!$I$6:$I$23,'S2'!$B$6:$B$23,$A56,'S2'!$E$6:$E$23,"Ambos")+SUMIFS('S3'!$I$6:$I$24,'S3'!$B$6:$B$24,$A56,'S3'!$E$6:$E$24,"Víctor")+SUMIFS('S3'!$I$6:$I$24,'S3'!$B$6:$B$24,$A56,'S3'!$E$6:$E$24,"Ambos")+SUMIFS('S4'!$I$6:$I$22,'S4'!$B$6:$B$22,$A56,'S4'!$E$6:$E$22,"Víctor")+SUMIFS('S4'!$I$6:$I$22,'S4'!$B$6:$B$22,$A56,'S4'!$E$6:$E$22,"Ambos")+SUMIFS('S5'!$I$6:$I$20,'S5'!$B$6:$B$20,$A56,'S5'!$E$6:$E$20,"Víctor")+SUMIFS('S5'!$I$6:$I$20,'S5'!$B$6:$B$20,$A56,'S5'!$E$6:$E$20,"Ambos")+SUMIFS('S6'!$I$6:$I$17,'S6'!$B$6:$B$17,$A56,'S6'!$E$6:$E$17,"Víctor")+SUMIFS('S6'!$I$6:$I$17,'S6'!$B$6:$B$17,$A56,'S6'!$E$6:$E$17,"Ambos")+SUMIFS('S7'!$I$6:$I$19,'S7'!$B$6:$B$19,$A56,'S7'!$E$6:$E$19,"Víctor")+SUMIFS('S7'!$I$6:$I$19,'S7'!$B$6:$B$19,$A56,'S7'!$E$6:$E$19,"Ambos")+SUMIFS('S8'!$I$6:$I$23,'S8'!$B$6:$B$23,$A56,'S8'!$E$6:$E$23,"Víctor")+SUMIFS('S8'!$I$6:$I$23,'S8'!$B$6:$B$23,$A56,'S8'!$E$6:$E$23,"Ambos")+SUMIFS('S9'!$I$6:$I$15,'S9'!$B$6:$B$15,$A56,'S9'!$E$6:$E$15,"Víctor")+SUMIFS('S9'!$I$6:$I$15,'S9'!$B$6:$B$15,$A56,'S9'!$E$6:$E$15,"Ambos")+SUMIFS('S10'!$I$6:$I$13,'S10'!$B$6:$B$13,$A56,'S10'!$E$6:$E$13,"Víctor")+SUMIFS('S10'!$I$6:$I$13,'S10'!$B$6:$B$13,$A56,'S10'!$E$6:$E$13,"Ambos")+SUMIFS('Holgura'!$I$6:$I$11,'Holgura'!$B$6:$B$11,$A56,'Holgura'!$E$6:$E$11,"Víctor")+SUMIFS('Holgura'!$I$6:$I$11,'Holgura'!$B$6:$B$11,$A56,'Holgura'!$E$6:$E$11,"Ambos")+SUMIFS('Entrega'!$I$6:$I$9,'Entrega'!$B$6:$B$9,$A56,'Entrega'!$E$6:$E$9,"Víctor")+SUMIFS('Entrega'!$I$6:$I$9,'Entrega'!$B$6:$B$9,$A56,'Entrega'!$E$6:$E$9,"Ambos")+SUMIFS('Defensa'!$I$6:$I$10,'Defensa'!$B$6:$B$10,$A56,'Defensa'!$E$6:$E$10,"Víctor")+SUMIFS('Defensa'!$I$6:$I$10,'Defensa'!$B$6:$B$10,$A56,'Defensa'!$E$6:$E$10,"Ambos")</f>
         <v/>
       </c>
       <c r="E56" s="21">
-        <f>SUMIFS('S1'!$I$6:$I$32,'S1'!$B$6:$B$32,$A56,'S1'!$E$6:$E$32,"Diego")+SUMIFS('S1'!$I$6:$I$32,'S1'!$B$6:$B$32,$A56,'S1'!$E$6:$E$32,"Ambos")+SUMIFS('S2'!$I$6:$I$23,'S2'!$B$6:$B$23,$A56,'S2'!$E$6:$E$23,"Diego")+SUMIFS('S2'!$I$6:$I$23,'S2'!$B$6:$B$23,$A56,'S2'!$E$6:$E$23,"Ambos")+SUMIFS('S3'!$I$6:$I$19,'S3'!$B$6:$B$19,$A56,'S3'!$E$6:$E$19,"Diego")+SUMIFS('S3'!$I$6:$I$19,'S3'!$B$6:$B$19,$A56,'S3'!$E$6:$E$19,"Ambos")+SUMIFS('S4'!$I$6:$I$20,'S4'!$B$6:$B$20,$A56,'S4'!$E$6:$E$20,"Diego")+SUMIFS('S4'!$I$6:$I$20,'S4'!$B$6:$B$20,$A56,'S4'!$E$6:$E$20,"Ambos")+SUMIFS('S5'!$I$6:$I$20,'S5'!$B$6:$B$20,$A56,'S5'!$E$6:$E$20,"Diego")+SUMIFS('S5'!$I$6:$I$20,'S5'!$B$6:$B$20,$A56,'S5'!$E$6:$E$20,"Ambos")+SUMIFS('S6'!$I$6:$I$17,'S6'!$B$6:$B$17,$A56,'S6'!$E$6:$E$17,"Diego")+SUMIFS('S6'!$I$6:$I$17,'S6'!$B$6:$B$17,$A56,'S6'!$E$6:$E$17,"Ambos")+SUMIFS('S7'!$I$6:$I$19,'S7'!$B$6:$B$19,$A56,'S7'!$E$6:$E$19,"Diego")+SUMIFS('S7'!$I$6:$I$19,'S7'!$B$6:$B$19,$A56,'S7'!$E$6:$E$19,"Ambos")+SUMIFS('S8'!$I$6:$I$23,'S8'!$B$6:$B$23,$A56,'S8'!$E$6:$E$23,"Diego")+SUMIFS('S8'!$I$6:$I$23,'S8'!$B$6:$B$23,$A56,'S8'!$E$6:$E$23,"Ambos")+SUMIFS('S9'!$I$6:$I$15,'S9'!$B$6:$B$15,$A56,'S9'!$E$6:$E$15,"Diego")+SUMIFS('S9'!$I$6:$I$15,'S9'!$B$6:$B$15,$A56,'S9'!$E$6:$E$15,"Ambos")+SUMIFS('S10'!$I$6:$I$13,'S10'!$B$6:$B$13,$A56,'S10'!$E$6:$E$13,"Diego")+SUMIFS('S10'!$I$6:$I$13,'S10'!$B$6:$B$13,$A56,'S10'!$E$6:$E$13,"Ambos")+SUMIFS('Holgura'!$I$6:$I$11,'Holgura'!$B$6:$B$11,$A56,'Holgura'!$E$6:$E$11,"Diego")+SUMIFS('Holgura'!$I$6:$I$11,'Holgura'!$B$6:$B$11,$A56,'Holgura'!$E$6:$E$11,"Ambos")+SUMIFS('Entrega'!$I$6:$I$9,'Entrega'!$B$6:$B$9,$A56,'Entrega'!$E$6:$E$9,"Diego")+SUMIFS('Entrega'!$I$6:$I$9,'Entrega'!$B$6:$B$9,$A56,'Entrega'!$E$6:$E$9,"Ambos")+SUMIFS('Defensa'!$I$6:$I$10,'Defensa'!$B$6:$B$10,$A56,'Defensa'!$E$6:$E$10,"Diego")+SUMIFS('Defensa'!$I$6:$I$10,'Defensa'!$B$6:$B$10,$A56,'Defensa'!$E$6:$E$10,"Ambos")</f>
+        <f>SUMIFS('S1'!$I$6:$I$32,'S1'!$B$6:$B$32,$A56,'S1'!$E$6:$E$32,"Diego")+SUMIFS('S1'!$I$6:$I$32,'S1'!$B$6:$B$32,$A56,'S1'!$E$6:$E$32,"Ambos")+SUMIFS('S2'!$I$6:$I$23,'S2'!$B$6:$B$23,$A56,'S2'!$E$6:$E$23,"Diego")+SUMIFS('S2'!$I$6:$I$23,'S2'!$B$6:$B$23,$A56,'S2'!$E$6:$E$23,"Ambos")+SUMIFS('S3'!$I$6:$I$24,'S3'!$B$6:$B$24,$A56,'S3'!$E$6:$E$24,"Diego")+SUMIFS('S3'!$I$6:$I$24,'S3'!$B$6:$B$24,$A56,'S3'!$E$6:$E$24,"Ambos")+SUMIFS('S4'!$I$6:$I$22,'S4'!$B$6:$B$22,$A56,'S4'!$E$6:$E$22,"Diego")+SUMIFS('S4'!$I$6:$I$22,'S4'!$B$6:$B$22,$A56,'S4'!$E$6:$E$22,"Ambos")+SUMIFS('S5'!$I$6:$I$20,'S5'!$B$6:$B$20,$A56,'S5'!$E$6:$E$20,"Diego")+SUMIFS('S5'!$I$6:$I$20,'S5'!$B$6:$B$20,$A56,'S5'!$E$6:$E$20,"Ambos")+SUMIFS('S6'!$I$6:$I$17,'S6'!$B$6:$B$17,$A56,'S6'!$E$6:$E$17,"Diego")+SUMIFS('S6'!$I$6:$I$17,'S6'!$B$6:$B$17,$A56,'S6'!$E$6:$E$17,"Ambos")+SUMIFS('S7'!$I$6:$I$19,'S7'!$B$6:$B$19,$A56,'S7'!$E$6:$E$19,"Diego")+SUMIFS('S7'!$I$6:$I$19,'S7'!$B$6:$B$19,$A56,'S7'!$E$6:$E$19,"Ambos")+SUMIFS('S8'!$I$6:$I$23,'S8'!$B$6:$B$23,$A56,'S8'!$E$6:$E$23,"Diego")+SUMIFS('S8'!$I$6:$I$23,'S8'!$B$6:$B$23,$A56,'S8'!$E$6:$E$23,"Ambos")+SUMIFS('S9'!$I$6:$I$15,'S9'!$B$6:$B$15,$A56,'S9'!$E$6:$E$15,"Diego")+SUMIFS('S9'!$I$6:$I$15,'S9'!$B$6:$B$15,$A56,'S9'!$E$6:$E$15,"Ambos")+SUMIFS('S10'!$I$6:$I$13,'S10'!$B$6:$B$13,$A56,'S10'!$E$6:$E$13,"Diego")+SUMIFS('S10'!$I$6:$I$13,'S10'!$B$6:$B$13,$A56,'S10'!$E$6:$E$13,"Ambos")+SUMIFS('Holgura'!$I$6:$I$11,'Holgura'!$B$6:$B$11,$A56,'Holgura'!$E$6:$E$11,"Diego")+SUMIFS('Holgura'!$I$6:$I$11,'Holgura'!$B$6:$B$11,$A56,'Holgura'!$E$6:$E$11,"Ambos")+SUMIFS('Entrega'!$I$6:$I$9,'Entrega'!$B$6:$B$9,$A56,'Entrega'!$E$6:$E$9,"Diego")+SUMIFS('Entrega'!$I$6:$I$9,'Entrega'!$B$6:$B$9,$A56,'Entrega'!$E$6:$E$9,"Ambos")+SUMIFS('Defensa'!$I$6:$I$10,'Defensa'!$B$6:$B$10,$A56,'Defensa'!$E$6:$E$10,"Diego")+SUMIFS('Defensa'!$I$6:$I$10,'Defensa'!$B$6:$B$10,$A56,'Defensa'!$E$6:$E$10,"Ambos")</f>
         <v/>
       </c>
       <c r="F56" s="21">
-        <f>COUNTIFS('S1'!$B$6:$B$32,$A56,'S1'!$E$6:$E$32,"Víctor")+COUNTIFS('S1'!$B$6:$B$32,$A56,'S1'!$E$6:$E$32,"Ambos")+COUNTIFS('S2'!$B$6:$B$23,$A56,'S2'!$E$6:$E$23,"Víctor")+COUNTIFS('S2'!$B$6:$B$23,$A56,'S2'!$E$6:$E$23,"Ambos")+COUNTIFS('S3'!$B$6:$B$19,$A56,'S3'!$E$6:$E$19,"Víctor")+COUNTIFS('S3'!$B$6:$B$19,$A56,'S3'!$E$6:$E$19,"Ambos")+COUNTIFS('S4'!$B$6:$B$20,$A56,'S4'!$E$6:$E$20,"Víctor")+COUNTIFS('S4'!$B$6:$B$20,$A56,'S4'!$E$6:$E$20,"Ambos")+COUNTIFS('S5'!$B$6:$B$20,$A56,'S5'!$E$6:$E$20,"Víctor")+COUNTIFS('S5'!$B$6:$B$20,$A56,'S5'!$E$6:$E$20,"Ambos")+COUNTIFS('S6'!$B$6:$B$17,$A56,'S6'!$E$6:$E$17,"Víctor")+COUNTIFS('S6'!$B$6:$B$17,$A56,'S6'!$E$6:$E$17,"Ambos")+COUNTIFS('S7'!$B$6:$B$19,$A56,'S7'!$E$6:$E$19,"Víctor")+COUNTIFS('S7'!$B$6:$B$19,$A56,'S7'!$E$6:$E$19,"Ambos")+COUNTIFS('S8'!$B$6:$B$23,$A56,'S8'!$E$6:$E$23,"Víctor")+COUNTIFS('S8'!$B$6:$B$23,$A56,'S8'!$E$6:$E$23,"Ambos")+COUNTIFS('S9'!$B$6:$B$15,$A56,'S9'!$E$6:$E$15,"Víctor")+COUNTIFS('S9'!$B$6:$B$15,$A56,'S9'!$E$6:$E$15,"Ambos")+COUNTIFS('S10'!$B$6:$B$13,$A56,'S10'!$E$6:$E$13,"Víctor")+COUNTIFS('S10'!$B$6:$B$13,$A56,'S10'!$E$6:$E$13,"Ambos")+COUNTIFS('Holgura'!$B$6:$B$11,$A56,'Holgura'!$E$6:$E$11,"Víctor")+COUNTIFS('Holgura'!$B$6:$B$11,$A56,'Holgura'!$E$6:$E$11,"Ambos")+COUNTIFS('Entrega'!$B$6:$B$9,$A56,'Entrega'!$E$6:$E$9,"Víctor")+COUNTIFS('Entrega'!$B$6:$B$9,$A56,'Entrega'!$E$6:$E$9,"Ambos")+COUNTIFS('Defensa'!$B$6:$B$10,$A56,'Defensa'!$E$6:$E$10,"Víctor")+COUNTIFS('Defensa'!$B$6:$B$10,$A56,'Defensa'!$E$6:$E$10,"Ambos")</f>
+        <f>COUNTIFS('S1'!$B$6:$B$32,$A56,'S1'!$E$6:$E$32,"Víctor")+COUNTIFS('S1'!$B$6:$B$32,$A56,'S1'!$E$6:$E$32,"Ambos")+COUNTIFS('S2'!$B$6:$B$23,$A56,'S2'!$E$6:$E$23,"Víctor")+COUNTIFS('S2'!$B$6:$B$23,$A56,'S2'!$E$6:$E$23,"Ambos")+COUNTIFS('S3'!$B$6:$B$24,$A56,'S3'!$E$6:$E$24,"Víctor")+COUNTIFS('S3'!$B$6:$B$24,$A56,'S3'!$E$6:$E$24,"Ambos")+COUNTIFS('S4'!$B$6:$B$22,$A56,'S4'!$E$6:$E$22,"Víctor")+COUNTIFS('S4'!$B$6:$B$22,$A56,'S4'!$E$6:$E$22,"Ambos")+COUNTIFS('S5'!$B$6:$B$20,$A56,'S5'!$E$6:$E$20,"Víctor")+COUNTIFS('S5'!$B$6:$B$20,$A56,'S5'!$E$6:$E$20,"Ambos")+COUNTIFS('S6'!$B$6:$B$17,$A56,'S6'!$E$6:$E$17,"Víctor")+COUNTIFS('S6'!$B$6:$B$17,$A56,'S6'!$E$6:$E$17,"Ambos")+COUNTIFS('S7'!$B$6:$B$19,$A56,'S7'!$E$6:$E$19,"Víctor")+COUNTIFS('S7'!$B$6:$B$19,$A56,'S7'!$E$6:$E$19,"Ambos")+COUNTIFS('S8'!$B$6:$B$23,$A56,'S8'!$E$6:$E$23,"Víctor")+COUNTIFS('S8'!$B$6:$B$23,$A56,'S8'!$E$6:$E$23,"Ambos")+COUNTIFS('S9'!$B$6:$B$15,$A56,'S9'!$E$6:$E$15,"Víctor")+COUNTIFS('S9'!$B$6:$B$15,$A56,'S9'!$E$6:$E$15,"Ambos")+COUNTIFS('S10'!$B$6:$B$13,$A56,'S10'!$E$6:$E$13,"Víctor")+COUNTIFS('S10'!$B$6:$B$13,$A56,'S10'!$E$6:$E$13,"Ambos")+COUNTIFS('Holgura'!$B$6:$B$11,$A56,'Holgura'!$E$6:$E$11,"Víctor")+COUNTIFS('Holgura'!$B$6:$B$11,$A56,'Holgura'!$E$6:$E$11,"Ambos")+COUNTIFS('Entrega'!$B$6:$B$9,$A56,'Entrega'!$E$6:$E$9,"Víctor")+COUNTIFS('Entrega'!$B$6:$B$9,$A56,'Entrega'!$E$6:$E$9,"Ambos")+COUNTIFS('Defensa'!$B$6:$B$10,$A56,'Defensa'!$E$6:$E$10,"Víctor")+COUNTIFS('Defensa'!$B$6:$B$10,$A56,'Defensa'!$E$6:$E$10,"Ambos")</f>
         <v/>
       </c>
       <c r="G56" s="21">
-        <f>COUNTIFS('S1'!$B$6:$B$32,$A56,'S1'!$E$6:$E$32,"Diego")+COUNTIFS('S1'!$B$6:$B$32,$A56,'S1'!$E$6:$E$32,"Ambos")+COUNTIFS('S2'!$B$6:$B$23,$A56,'S2'!$E$6:$E$23,"Diego")+COUNTIFS('S2'!$B$6:$B$23,$A56,'S2'!$E$6:$E$23,"Ambos")+COUNTIFS('S3'!$B$6:$B$19,$A56,'S3'!$E$6:$E$19,"Diego")+COUNTIFS('S3'!$B$6:$B$19,$A56,'S3'!$E$6:$E$19,"Ambos")+COUNTIFS('S4'!$B$6:$B$20,$A56,'S4'!$E$6:$E$20,"Diego")+COUNTIFS('S4'!$B$6:$B$20,$A56,'S4'!$E$6:$E$20,"Ambos")+COUNTIFS('S5'!$B$6:$B$20,$A56,'S5'!$E$6:$E$20,"Diego")+COUNTIFS('S5'!$B$6:$B$20,$A56,'S5'!$E$6:$E$20,"Ambos")+COUNTIFS('S6'!$B$6:$B$17,$A56,'S6'!$E$6:$E$17,"Diego")+COUNTIFS('S6'!$B$6:$B$17,$A56,'S6'!$E$6:$E$17,"Ambos")+COUNTIFS('S7'!$B$6:$B$19,$A56,'S7'!$E$6:$E$19,"Diego")+COUNTIFS('S7'!$B$6:$B$19,$A56,'S7'!$E$6:$E$19,"Ambos")+COUNTIFS('S8'!$B$6:$B$23,$A56,'S8'!$E$6:$E$23,"Diego")+COUNTIFS('S8'!$B$6:$B$23,$A56,'S8'!$E$6:$E$23,"Ambos")+COUNTIFS('S9'!$B$6:$B$15,$A56,'S9'!$E$6:$E$15,"Diego")+COUNTIFS('S9'!$B$6:$B$15,$A56,'S9'!$E$6:$E$15,"Ambos")+COUNTIFS('S10'!$B$6:$B$13,$A56,'S10'!$E$6:$E$13,"Diego")+COUNTIFS('S10'!$B$6:$B$13,$A56,'S10'!$E$6:$E$13,"Ambos")+COUNTIFS('Holgura'!$B$6:$B$11,$A56,'Holgura'!$E$6:$E$11,"Diego")+COUNTIFS('Holgura'!$B$6:$B$11,$A56,'Holgura'!$E$6:$E$11,"Ambos")+COUNTIFS('Entrega'!$B$6:$B$9,$A56,'Entrega'!$E$6:$E$9,"Diego")+COUNTIFS('Entrega'!$B$6:$B$9,$A56,'Entrega'!$E$6:$E$9,"Ambos")+COUNTIFS('Defensa'!$B$6:$B$10,$A56,'Defensa'!$E$6:$E$10,"Diego")+COUNTIFS('Defensa'!$B$6:$B$10,$A56,'Defensa'!$E$6:$E$10,"Ambos")</f>
+        <f>COUNTIFS('S1'!$B$6:$B$32,$A56,'S1'!$E$6:$E$32,"Diego")+COUNTIFS('S1'!$B$6:$B$32,$A56,'S1'!$E$6:$E$32,"Ambos")+COUNTIFS('S2'!$B$6:$B$23,$A56,'S2'!$E$6:$E$23,"Diego")+COUNTIFS('S2'!$B$6:$B$23,$A56,'S2'!$E$6:$E$23,"Ambos")+COUNTIFS('S3'!$B$6:$B$24,$A56,'S3'!$E$6:$E$24,"Diego")+COUNTIFS('S3'!$B$6:$B$24,$A56,'S3'!$E$6:$E$24,"Ambos")+COUNTIFS('S4'!$B$6:$B$22,$A56,'S4'!$E$6:$E$22,"Diego")+COUNTIFS('S4'!$B$6:$B$22,$A56,'S4'!$E$6:$E$22,"Ambos")+COUNTIFS('S5'!$B$6:$B$20,$A56,'S5'!$E$6:$E$20,"Diego")+COUNTIFS('S5'!$B$6:$B$20,$A56,'S5'!$E$6:$E$20,"Ambos")+COUNTIFS('S6'!$B$6:$B$17,$A56,'S6'!$E$6:$E$17,"Diego")+COUNTIFS('S6'!$B$6:$B$17,$A56,'S6'!$E$6:$E$17,"Ambos")+COUNTIFS('S7'!$B$6:$B$19,$A56,'S7'!$E$6:$E$19,"Diego")+COUNTIFS('S7'!$B$6:$B$19,$A56,'S7'!$E$6:$E$19,"Ambos")+COUNTIFS('S8'!$B$6:$B$23,$A56,'S8'!$E$6:$E$23,"Diego")+COUNTIFS('S8'!$B$6:$B$23,$A56,'S8'!$E$6:$E$23,"Ambos")+COUNTIFS('S9'!$B$6:$B$15,$A56,'S9'!$E$6:$E$15,"Diego")+COUNTIFS('S9'!$B$6:$B$15,$A56,'S9'!$E$6:$E$15,"Ambos")+COUNTIFS('S10'!$B$6:$B$13,$A56,'S10'!$E$6:$E$13,"Diego")+COUNTIFS('S10'!$B$6:$B$13,$A56,'S10'!$E$6:$E$13,"Ambos")+COUNTIFS('Holgura'!$B$6:$B$11,$A56,'Holgura'!$E$6:$E$11,"Diego")+COUNTIFS('Holgura'!$B$6:$B$11,$A56,'Holgura'!$E$6:$E$11,"Ambos")+COUNTIFS('Entrega'!$B$6:$B$9,$A56,'Entrega'!$E$6:$E$9,"Diego")+COUNTIFS('Entrega'!$B$6:$B$9,$A56,'Entrega'!$E$6:$E$9,"Ambos")+COUNTIFS('Defensa'!$B$6:$B$10,$A56,'Defensa'!$E$6:$E$10,"Diego")+COUNTIFS('Defensa'!$B$6:$B$10,$A56,'Defensa'!$E$6:$E$10,"Ambos")</f>
         <v/>
       </c>
     </row>
@@ -10188,19 +10209,19 @@
         <v/>
       </c>
       <c r="D57" s="21">
-        <f>SUMIFS('S1'!$I$6:$I$32,'S1'!$B$6:$B$32,$A57,'S1'!$E$6:$E$32,"Víctor")+SUMIFS('S1'!$I$6:$I$32,'S1'!$B$6:$B$32,$A57,'S1'!$E$6:$E$32,"Ambos")+SUMIFS('S2'!$I$6:$I$23,'S2'!$B$6:$B$23,$A57,'S2'!$E$6:$E$23,"Víctor")+SUMIFS('S2'!$I$6:$I$23,'S2'!$B$6:$B$23,$A57,'S2'!$E$6:$E$23,"Ambos")+SUMIFS('S3'!$I$6:$I$19,'S3'!$B$6:$B$19,$A57,'S3'!$E$6:$E$19,"Víctor")+SUMIFS('S3'!$I$6:$I$19,'S3'!$B$6:$B$19,$A57,'S3'!$E$6:$E$19,"Ambos")+SUMIFS('S4'!$I$6:$I$20,'S4'!$B$6:$B$20,$A57,'S4'!$E$6:$E$20,"Víctor")+SUMIFS('S4'!$I$6:$I$20,'S4'!$B$6:$B$20,$A57,'S4'!$E$6:$E$20,"Ambos")+SUMIFS('S5'!$I$6:$I$20,'S5'!$B$6:$B$20,$A57,'S5'!$E$6:$E$20,"Víctor")+SUMIFS('S5'!$I$6:$I$20,'S5'!$B$6:$B$20,$A57,'S5'!$E$6:$E$20,"Ambos")+SUMIFS('S6'!$I$6:$I$17,'S6'!$B$6:$B$17,$A57,'S6'!$E$6:$E$17,"Víctor")+SUMIFS('S6'!$I$6:$I$17,'S6'!$B$6:$B$17,$A57,'S6'!$E$6:$E$17,"Ambos")+SUMIFS('S7'!$I$6:$I$19,'S7'!$B$6:$B$19,$A57,'S7'!$E$6:$E$19,"Víctor")+SUMIFS('S7'!$I$6:$I$19,'S7'!$B$6:$B$19,$A57,'S7'!$E$6:$E$19,"Ambos")+SUMIFS('S8'!$I$6:$I$23,'S8'!$B$6:$B$23,$A57,'S8'!$E$6:$E$23,"Víctor")+SUMIFS('S8'!$I$6:$I$23,'S8'!$B$6:$B$23,$A57,'S8'!$E$6:$E$23,"Ambos")+SUMIFS('S9'!$I$6:$I$15,'S9'!$B$6:$B$15,$A57,'S9'!$E$6:$E$15,"Víctor")+SUMIFS('S9'!$I$6:$I$15,'S9'!$B$6:$B$15,$A57,'S9'!$E$6:$E$15,"Ambos")+SUMIFS('S10'!$I$6:$I$13,'S10'!$B$6:$B$13,$A57,'S10'!$E$6:$E$13,"Víctor")+SUMIFS('S10'!$I$6:$I$13,'S10'!$B$6:$B$13,$A57,'S10'!$E$6:$E$13,"Ambos")+SUMIFS('Holgura'!$I$6:$I$11,'Holgura'!$B$6:$B$11,$A57,'Holgura'!$E$6:$E$11,"Víctor")+SUMIFS('Holgura'!$I$6:$I$11,'Holgura'!$B$6:$B$11,$A57,'Holgura'!$E$6:$E$11,"Ambos")+SUMIFS('Entrega'!$I$6:$I$9,'Entrega'!$B$6:$B$9,$A57,'Entrega'!$E$6:$E$9,"Víctor")+SUMIFS('Entrega'!$I$6:$I$9,'Entrega'!$B$6:$B$9,$A57,'Entrega'!$E$6:$E$9,"Ambos")+SUMIFS('Defensa'!$I$6:$I$10,'Defensa'!$B$6:$B$10,$A57,'Defensa'!$E$6:$E$10,"Víctor")+SUMIFS('Defensa'!$I$6:$I$10,'Defensa'!$B$6:$B$10,$A57,'Defensa'!$E$6:$E$10,"Ambos")</f>
+        <f>SUMIFS('S1'!$I$6:$I$32,'S1'!$B$6:$B$32,$A57,'S1'!$E$6:$E$32,"Víctor")+SUMIFS('S1'!$I$6:$I$32,'S1'!$B$6:$B$32,$A57,'S1'!$E$6:$E$32,"Ambos")+SUMIFS('S2'!$I$6:$I$23,'S2'!$B$6:$B$23,$A57,'S2'!$E$6:$E$23,"Víctor")+SUMIFS('S2'!$I$6:$I$23,'S2'!$B$6:$B$23,$A57,'S2'!$E$6:$E$23,"Ambos")+SUMIFS('S3'!$I$6:$I$24,'S3'!$B$6:$B$24,$A57,'S3'!$E$6:$E$24,"Víctor")+SUMIFS('S3'!$I$6:$I$24,'S3'!$B$6:$B$24,$A57,'S3'!$E$6:$E$24,"Ambos")+SUMIFS('S4'!$I$6:$I$22,'S4'!$B$6:$B$22,$A57,'S4'!$E$6:$E$22,"Víctor")+SUMIFS('S4'!$I$6:$I$22,'S4'!$B$6:$B$22,$A57,'S4'!$E$6:$E$22,"Ambos")+SUMIFS('S5'!$I$6:$I$20,'S5'!$B$6:$B$20,$A57,'S5'!$E$6:$E$20,"Víctor")+SUMIFS('S5'!$I$6:$I$20,'S5'!$B$6:$B$20,$A57,'S5'!$E$6:$E$20,"Ambos")+SUMIFS('S6'!$I$6:$I$17,'S6'!$B$6:$B$17,$A57,'S6'!$E$6:$E$17,"Víctor")+SUMIFS('S6'!$I$6:$I$17,'S6'!$B$6:$B$17,$A57,'S6'!$E$6:$E$17,"Ambos")+SUMIFS('S7'!$I$6:$I$19,'S7'!$B$6:$B$19,$A57,'S7'!$E$6:$E$19,"Víctor")+SUMIFS('S7'!$I$6:$I$19,'S7'!$B$6:$B$19,$A57,'S7'!$E$6:$E$19,"Ambos")+SUMIFS('S8'!$I$6:$I$23,'S8'!$B$6:$B$23,$A57,'S8'!$E$6:$E$23,"Víctor")+SUMIFS('S8'!$I$6:$I$23,'S8'!$B$6:$B$23,$A57,'S8'!$E$6:$E$23,"Ambos")+SUMIFS('S9'!$I$6:$I$15,'S9'!$B$6:$B$15,$A57,'S9'!$E$6:$E$15,"Víctor")+SUMIFS('S9'!$I$6:$I$15,'S9'!$B$6:$B$15,$A57,'S9'!$E$6:$E$15,"Ambos")+SUMIFS('S10'!$I$6:$I$13,'S10'!$B$6:$B$13,$A57,'S10'!$E$6:$E$13,"Víctor")+SUMIFS('S10'!$I$6:$I$13,'S10'!$B$6:$B$13,$A57,'S10'!$E$6:$E$13,"Ambos")+SUMIFS('Holgura'!$I$6:$I$11,'Holgura'!$B$6:$B$11,$A57,'Holgura'!$E$6:$E$11,"Víctor")+SUMIFS('Holgura'!$I$6:$I$11,'Holgura'!$B$6:$B$11,$A57,'Holgura'!$E$6:$E$11,"Ambos")+SUMIFS('Entrega'!$I$6:$I$9,'Entrega'!$B$6:$B$9,$A57,'Entrega'!$E$6:$E$9,"Víctor")+SUMIFS('Entrega'!$I$6:$I$9,'Entrega'!$B$6:$B$9,$A57,'Entrega'!$E$6:$E$9,"Ambos")+SUMIFS('Defensa'!$I$6:$I$10,'Defensa'!$B$6:$B$10,$A57,'Defensa'!$E$6:$E$10,"Víctor")+SUMIFS('Defensa'!$I$6:$I$10,'Defensa'!$B$6:$B$10,$A57,'Defensa'!$E$6:$E$10,"Ambos")</f>
         <v/>
       </c>
       <c r="E57" s="21">
-        <f>SUMIFS('S1'!$I$6:$I$32,'S1'!$B$6:$B$32,$A57,'S1'!$E$6:$E$32,"Diego")+SUMIFS('S1'!$I$6:$I$32,'S1'!$B$6:$B$32,$A57,'S1'!$E$6:$E$32,"Ambos")+SUMIFS('S2'!$I$6:$I$23,'S2'!$B$6:$B$23,$A57,'S2'!$E$6:$E$23,"Diego")+SUMIFS('S2'!$I$6:$I$23,'S2'!$B$6:$B$23,$A57,'S2'!$E$6:$E$23,"Ambos")+SUMIFS('S3'!$I$6:$I$19,'S3'!$B$6:$B$19,$A57,'S3'!$E$6:$E$19,"Diego")+SUMIFS('S3'!$I$6:$I$19,'S3'!$B$6:$B$19,$A57,'S3'!$E$6:$E$19,"Ambos")+SUMIFS('S4'!$I$6:$I$20,'S4'!$B$6:$B$20,$A57,'S4'!$E$6:$E$20,"Diego")+SUMIFS('S4'!$I$6:$I$20,'S4'!$B$6:$B$20,$A57,'S4'!$E$6:$E$20,"Ambos")+SUMIFS('S5'!$I$6:$I$20,'S5'!$B$6:$B$20,$A57,'S5'!$E$6:$E$20,"Diego")+SUMIFS('S5'!$I$6:$I$20,'S5'!$B$6:$B$20,$A57,'S5'!$E$6:$E$20,"Ambos")+SUMIFS('S6'!$I$6:$I$17,'S6'!$B$6:$B$17,$A57,'S6'!$E$6:$E$17,"Diego")+SUMIFS('S6'!$I$6:$I$17,'S6'!$B$6:$B$17,$A57,'S6'!$E$6:$E$17,"Ambos")+SUMIFS('S7'!$I$6:$I$19,'S7'!$B$6:$B$19,$A57,'S7'!$E$6:$E$19,"Diego")+SUMIFS('S7'!$I$6:$I$19,'S7'!$B$6:$B$19,$A57,'S7'!$E$6:$E$19,"Ambos")+SUMIFS('S8'!$I$6:$I$23,'S8'!$B$6:$B$23,$A57,'S8'!$E$6:$E$23,"Diego")+SUMIFS('S8'!$I$6:$I$23,'S8'!$B$6:$B$23,$A57,'S8'!$E$6:$E$23,"Ambos")+SUMIFS('S9'!$I$6:$I$15,'S9'!$B$6:$B$15,$A57,'S9'!$E$6:$E$15,"Diego")+SUMIFS('S9'!$I$6:$I$15,'S9'!$B$6:$B$15,$A57,'S9'!$E$6:$E$15,"Ambos")+SUMIFS('S10'!$I$6:$I$13,'S10'!$B$6:$B$13,$A57,'S10'!$E$6:$E$13,"Diego")+SUMIFS('S10'!$I$6:$I$13,'S10'!$B$6:$B$13,$A57,'S10'!$E$6:$E$13,"Ambos")+SUMIFS('Holgura'!$I$6:$I$11,'Holgura'!$B$6:$B$11,$A57,'Holgura'!$E$6:$E$11,"Diego")+SUMIFS('Holgura'!$I$6:$I$11,'Holgura'!$B$6:$B$11,$A57,'Holgura'!$E$6:$E$11,"Ambos")+SUMIFS('Entrega'!$I$6:$I$9,'Entrega'!$B$6:$B$9,$A57,'Entrega'!$E$6:$E$9,"Diego")+SUMIFS('Entrega'!$I$6:$I$9,'Entrega'!$B$6:$B$9,$A57,'Entrega'!$E$6:$E$9,"Ambos")+SUMIFS('Defensa'!$I$6:$I$10,'Defensa'!$B$6:$B$10,$A57,'Defensa'!$E$6:$E$10,"Diego")+SUMIFS('Defensa'!$I$6:$I$10,'Defensa'!$B$6:$B$10,$A57,'Defensa'!$E$6:$E$10,"Ambos")</f>
+        <f>SUMIFS('S1'!$I$6:$I$32,'S1'!$B$6:$B$32,$A57,'S1'!$E$6:$E$32,"Diego")+SUMIFS('S1'!$I$6:$I$32,'S1'!$B$6:$B$32,$A57,'S1'!$E$6:$E$32,"Ambos")+SUMIFS('S2'!$I$6:$I$23,'S2'!$B$6:$B$23,$A57,'S2'!$E$6:$E$23,"Diego")+SUMIFS('S2'!$I$6:$I$23,'S2'!$B$6:$B$23,$A57,'S2'!$E$6:$E$23,"Ambos")+SUMIFS('S3'!$I$6:$I$24,'S3'!$B$6:$B$24,$A57,'S3'!$E$6:$E$24,"Diego")+SUMIFS('S3'!$I$6:$I$24,'S3'!$B$6:$B$24,$A57,'S3'!$E$6:$E$24,"Ambos")+SUMIFS('S4'!$I$6:$I$22,'S4'!$B$6:$B$22,$A57,'S4'!$E$6:$E$22,"Diego")+SUMIFS('S4'!$I$6:$I$22,'S4'!$B$6:$B$22,$A57,'S4'!$E$6:$E$22,"Ambos")+SUMIFS('S5'!$I$6:$I$20,'S5'!$B$6:$B$20,$A57,'S5'!$E$6:$E$20,"Diego")+SUMIFS('S5'!$I$6:$I$20,'S5'!$B$6:$B$20,$A57,'S5'!$E$6:$E$20,"Ambos")+SUMIFS('S6'!$I$6:$I$17,'S6'!$B$6:$B$17,$A57,'S6'!$E$6:$E$17,"Diego")+SUMIFS('S6'!$I$6:$I$17,'S6'!$B$6:$B$17,$A57,'S6'!$E$6:$E$17,"Ambos")+SUMIFS('S7'!$I$6:$I$19,'S7'!$B$6:$B$19,$A57,'S7'!$E$6:$E$19,"Diego")+SUMIFS('S7'!$I$6:$I$19,'S7'!$B$6:$B$19,$A57,'S7'!$E$6:$E$19,"Ambos")+SUMIFS('S8'!$I$6:$I$23,'S8'!$B$6:$B$23,$A57,'S8'!$E$6:$E$23,"Diego")+SUMIFS('S8'!$I$6:$I$23,'S8'!$B$6:$B$23,$A57,'S8'!$E$6:$E$23,"Ambos")+SUMIFS('S9'!$I$6:$I$15,'S9'!$B$6:$B$15,$A57,'S9'!$E$6:$E$15,"Diego")+SUMIFS('S9'!$I$6:$I$15,'S9'!$B$6:$B$15,$A57,'S9'!$E$6:$E$15,"Ambos")+SUMIFS('S10'!$I$6:$I$13,'S10'!$B$6:$B$13,$A57,'S10'!$E$6:$E$13,"Diego")+SUMIFS('S10'!$I$6:$I$13,'S10'!$B$6:$B$13,$A57,'S10'!$E$6:$E$13,"Ambos")+SUMIFS('Holgura'!$I$6:$I$11,'Holgura'!$B$6:$B$11,$A57,'Holgura'!$E$6:$E$11,"Diego")+SUMIFS('Holgura'!$I$6:$I$11,'Holgura'!$B$6:$B$11,$A57,'Holgura'!$E$6:$E$11,"Ambos")+SUMIFS('Entrega'!$I$6:$I$9,'Entrega'!$B$6:$B$9,$A57,'Entrega'!$E$6:$E$9,"Diego")+SUMIFS('Entrega'!$I$6:$I$9,'Entrega'!$B$6:$B$9,$A57,'Entrega'!$E$6:$E$9,"Ambos")+SUMIFS('Defensa'!$I$6:$I$10,'Defensa'!$B$6:$B$10,$A57,'Defensa'!$E$6:$E$10,"Diego")+SUMIFS('Defensa'!$I$6:$I$10,'Defensa'!$B$6:$B$10,$A57,'Defensa'!$E$6:$E$10,"Ambos")</f>
         <v/>
       </c>
       <c r="F57" s="21">
-        <f>COUNTIFS('S1'!$B$6:$B$32,$A57,'S1'!$E$6:$E$32,"Víctor")+COUNTIFS('S1'!$B$6:$B$32,$A57,'S1'!$E$6:$E$32,"Ambos")+COUNTIFS('S2'!$B$6:$B$23,$A57,'S2'!$E$6:$E$23,"Víctor")+COUNTIFS('S2'!$B$6:$B$23,$A57,'S2'!$E$6:$E$23,"Ambos")+COUNTIFS('S3'!$B$6:$B$19,$A57,'S3'!$E$6:$E$19,"Víctor")+COUNTIFS('S3'!$B$6:$B$19,$A57,'S3'!$E$6:$E$19,"Ambos")+COUNTIFS('S4'!$B$6:$B$20,$A57,'S4'!$E$6:$E$20,"Víctor")+COUNTIFS('S4'!$B$6:$B$20,$A57,'S4'!$E$6:$E$20,"Ambos")+COUNTIFS('S5'!$B$6:$B$20,$A57,'S5'!$E$6:$E$20,"Víctor")+COUNTIFS('S5'!$B$6:$B$20,$A57,'S5'!$E$6:$E$20,"Ambos")+COUNTIFS('S6'!$B$6:$B$17,$A57,'S6'!$E$6:$E$17,"Víctor")+COUNTIFS('S6'!$B$6:$B$17,$A57,'S6'!$E$6:$E$17,"Ambos")+COUNTIFS('S7'!$B$6:$B$19,$A57,'S7'!$E$6:$E$19,"Víctor")+COUNTIFS('S7'!$B$6:$B$19,$A57,'S7'!$E$6:$E$19,"Ambos")+COUNTIFS('S8'!$B$6:$B$23,$A57,'S8'!$E$6:$E$23,"Víctor")+COUNTIFS('S8'!$B$6:$B$23,$A57,'S8'!$E$6:$E$23,"Ambos")+COUNTIFS('S9'!$B$6:$B$15,$A57,'S9'!$E$6:$E$15,"Víctor")+COUNTIFS('S9'!$B$6:$B$15,$A57,'S9'!$E$6:$E$15,"Ambos")+COUNTIFS('S10'!$B$6:$B$13,$A57,'S10'!$E$6:$E$13,"Víctor")+COUNTIFS('S10'!$B$6:$B$13,$A57,'S10'!$E$6:$E$13,"Ambos")+COUNTIFS('Holgura'!$B$6:$B$11,$A57,'Holgura'!$E$6:$E$11,"Víctor")+COUNTIFS('Holgura'!$B$6:$B$11,$A57,'Holgura'!$E$6:$E$11,"Ambos")+COUNTIFS('Entrega'!$B$6:$B$9,$A57,'Entrega'!$E$6:$E$9,"Víctor")+COUNTIFS('Entrega'!$B$6:$B$9,$A57,'Entrega'!$E$6:$E$9,"Ambos")+COUNTIFS('Defensa'!$B$6:$B$10,$A57,'Defensa'!$E$6:$E$10,"Víctor")+COUNTIFS('Defensa'!$B$6:$B$10,$A57,'Defensa'!$E$6:$E$10,"Ambos")</f>
+        <f>COUNTIFS('S1'!$B$6:$B$32,$A57,'S1'!$E$6:$E$32,"Víctor")+COUNTIFS('S1'!$B$6:$B$32,$A57,'S1'!$E$6:$E$32,"Ambos")+COUNTIFS('S2'!$B$6:$B$23,$A57,'S2'!$E$6:$E$23,"Víctor")+COUNTIFS('S2'!$B$6:$B$23,$A57,'S2'!$E$6:$E$23,"Ambos")+COUNTIFS('S3'!$B$6:$B$24,$A57,'S3'!$E$6:$E$24,"Víctor")+COUNTIFS('S3'!$B$6:$B$24,$A57,'S3'!$E$6:$E$24,"Ambos")+COUNTIFS('S4'!$B$6:$B$22,$A57,'S4'!$E$6:$E$22,"Víctor")+COUNTIFS('S4'!$B$6:$B$22,$A57,'S4'!$E$6:$E$22,"Ambos")+COUNTIFS('S5'!$B$6:$B$20,$A57,'S5'!$E$6:$E$20,"Víctor")+COUNTIFS('S5'!$B$6:$B$20,$A57,'S5'!$E$6:$E$20,"Ambos")+COUNTIFS('S6'!$B$6:$B$17,$A57,'S6'!$E$6:$E$17,"Víctor")+COUNTIFS('S6'!$B$6:$B$17,$A57,'S6'!$E$6:$E$17,"Ambos")+COUNTIFS('S7'!$B$6:$B$19,$A57,'S7'!$E$6:$E$19,"Víctor")+COUNTIFS('S7'!$B$6:$B$19,$A57,'S7'!$E$6:$E$19,"Ambos")+COUNTIFS('S8'!$B$6:$B$23,$A57,'S8'!$E$6:$E$23,"Víctor")+COUNTIFS('S8'!$B$6:$B$23,$A57,'S8'!$E$6:$E$23,"Ambos")+COUNTIFS('S9'!$B$6:$B$15,$A57,'S9'!$E$6:$E$15,"Víctor")+COUNTIFS('S9'!$B$6:$B$15,$A57,'S9'!$E$6:$E$15,"Ambos")+COUNTIFS('S10'!$B$6:$B$13,$A57,'S10'!$E$6:$E$13,"Víctor")+COUNTIFS('S10'!$B$6:$B$13,$A57,'S10'!$E$6:$E$13,"Ambos")+COUNTIFS('Holgura'!$B$6:$B$11,$A57,'Holgura'!$E$6:$E$11,"Víctor")+COUNTIFS('Holgura'!$B$6:$B$11,$A57,'Holgura'!$E$6:$E$11,"Ambos")+COUNTIFS('Entrega'!$B$6:$B$9,$A57,'Entrega'!$E$6:$E$9,"Víctor")+COUNTIFS('Entrega'!$B$6:$B$9,$A57,'Entrega'!$E$6:$E$9,"Ambos")+COUNTIFS('Defensa'!$B$6:$B$10,$A57,'Defensa'!$E$6:$E$10,"Víctor")+COUNTIFS('Defensa'!$B$6:$B$10,$A57,'Defensa'!$E$6:$E$10,"Ambos")</f>
         <v/>
       </c>
       <c r="G57" s="21">
-        <f>COUNTIFS('S1'!$B$6:$B$32,$A57,'S1'!$E$6:$E$32,"Diego")+COUNTIFS('S1'!$B$6:$B$32,$A57,'S1'!$E$6:$E$32,"Ambos")+COUNTIFS('S2'!$B$6:$B$23,$A57,'S2'!$E$6:$E$23,"Diego")+COUNTIFS('S2'!$B$6:$B$23,$A57,'S2'!$E$6:$E$23,"Ambos")+COUNTIFS('S3'!$B$6:$B$19,$A57,'S3'!$E$6:$E$19,"Diego")+COUNTIFS('S3'!$B$6:$B$19,$A57,'S3'!$E$6:$E$19,"Ambos")+COUNTIFS('S4'!$B$6:$B$20,$A57,'S4'!$E$6:$E$20,"Diego")+COUNTIFS('S4'!$B$6:$B$20,$A57,'S4'!$E$6:$E$20,"Ambos")+COUNTIFS('S5'!$B$6:$B$20,$A57,'S5'!$E$6:$E$20,"Diego")+COUNTIFS('S5'!$B$6:$B$20,$A57,'S5'!$E$6:$E$20,"Ambos")+COUNTIFS('S6'!$B$6:$B$17,$A57,'S6'!$E$6:$E$17,"Diego")+COUNTIFS('S6'!$B$6:$B$17,$A57,'S6'!$E$6:$E$17,"Ambos")+COUNTIFS('S7'!$B$6:$B$19,$A57,'S7'!$E$6:$E$19,"Diego")+COUNTIFS('S7'!$B$6:$B$19,$A57,'S7'!$E$6:$E$19,"Ambos")+COUNTIFS('S8'!$B$6:$B$23,$A57,'S8'!$E$6:$E$23,"Diego")+COUNTIFS('S8'!$B$6:$B$23,$A57,'S8'!$E$6:$E$23,"Ambos")+COUNTIFS('S9'!$B$6:$B$15,$A57,'S9'!$E$6:$E$15,"Diego")+COUNTIFS('S9'!$B$6:$B$15,$A57,'S9'!$E$6:$E$15,"Ambos")+COUNTIFS('S10'!$B$6:$B$13,$A57,'S10'!$E$6:$E$13,"Diego")+COUNTIFS('S10'!$B$6:$B$13,$A57,'S10'!$E$6:$E$13,"Ambos")+COUNTIFS('Holgura'!$B$6:$B$11,$A57,'Holgura'!$E$6:$E$11,"Diego")+COUNTIFS('Holgura'!$B$6:$B$11,$A57,'Holgura'!$E$6:$E$11,"Ambos")+COUNTIFS('Entrega'!$B$6:$B$9,$A57,'Entrega'!$E$6:$E$9,"Diego")+COUNTIFS('Entrega'!$B$6:$B$9,$A57,'Entrega'!$E$6:$E$9,"Ambos")+COUNTIFS('Defensa'!$B$6:$B$10,$A57,'Defensa'!$E$6:$E$10,"Diego")+COUNTIFS('Defensa'!$B$6:$B$10,$A57,'Defensa'!$E$6:$E$10,"Ambos")</f>
+        <f>COUNTIFS('S1'!$B$6:$B$32,$A57,'S1'!$E$6:$E$32,"Diego")+COUNTIFS('S1'!$B$6:$B$32,$A57,'S1'!$E$6:$E$32,"Ambos")+COUNTIFS('S2'!$B$6:$B$23,$A57,'S2'!$E$6:$E$23,"Diego")+COUNTIFS('S2'!$B$6:$B$23,$A57,'S2'!$E$6:$E$23,"Ambos")+COUNTIFS('S3'!$B$6:$B$24,$A57,'S3'!$E$6:$E$24,"Diego")+COUNTIFS('S3'!$B$6:$B$24,$A57,'S3'!$E$6:$E$24,"Ambos")+COUNTIFS('S4'!$B$6:$B$22,$A57,'S4'!$E$6:$E$22,"Diego")+COUNTIFS('S4'!$B$6:$B$22,$A57,'S4'!$E$6:$E$22,"Ambos")+COUNTIFS('S5'!$B$6:$B$20,$A57,'S5'!$E$6:$E$20,"Diego")+COUNTIFS('S5'!$B$6:$B$20,$A57,'S5'!$E$6:$E$20,"Ambos")+COUNTIFS('S6'!$B$6:$B$17,$A57,'S6'!$E$6:$E$17,"Diego")+COUNTIFS('S6'!$B$6:$B$17,$A57,'S6'!$E$6:$E$17,"Ambos")+COUNTIFS('S7'!$B$6:$B$19,$A57,'S7'!$E$6:$E$19,"Diego")+COUNTIFS('S7'!$B$6:$B$19,$A57,'S7'!$E$6:$E$19,"Ambos")+COUNTIFS('S8'!$B$6:$B$23,$A57,'S8'!$E$6:$E$23,"Diego")+COUNTIFS('S8'!$B$6:$B$23,$A57,'S8'!$E$6:$E$23,"Ambos")+COUNTIFS('S9'!$B$6:$B$15,$A57,'S9'!$E$6:$E$15,"Diego")+COUNTIFS('S9'!$B$6:$B$15,$A57,'S9'!$E$6:$E$15,"Ambos")+COUNTIFS('S10'!$B$6:$B$13,$A57,'S10'!$E$6:$E$13,"Diego")+COUNTIFS('S10'!$B$6:$B$13,$A57,'S10'!$E$6:$E$13,"Ambos")+COUNTIFS('Holgura'!$B$6:$B$11,$A57,'Holgura'!$E$6:$E$11,"Diego")+COUNTIFS('Holgura'!$B$6:$B$11,$A57,'Holgura'!$E$6:$E$11,"Ambos")+COUNTIFS('Entrega'!$B$6:$B$9,$A57,'Entrega'!$E$6:$E$9,"Diego")+COUNTIFS('Entrega'!$B$6:$B$9,$A57,'Entrega'!$E$6:$E$9,"Ambos")+COUNTIFS('Defensa'!$B$6:$B$10,$A57,'Defensa'!$E$6:$E$10,"Diego")+COUNTIFS('Defensa'!$B$6:$B$10,$A57,'Defensa'!$E$6:$E$10,"Ambos")</f>
         <v/>
       </c>
     </row>
@@ -10217,19 +10238,19 @@
         <v/>
       </c>
       <c r="D58" s="21">
-        <f>SUMIFS('S1'!$I$6:$I$32,'S1'!$B$6:$B$32,$A58,'S1'!$E$6:$E$32,"Víctor")+SUMIFS('S1'!$I$6:$I$32,'S1'!$B$6:$B$32,$A58,'S1'!$E$6:$E$32,"Ambos")+SUMIFS('S2'!$I$6:$I$23,'S2'!$B$6:$B$23,$A58,'S2'!$E$6:$E$23,"Víctor")+SUMIFS('S2'!$I$6:$I$23,'S2'!$B$6:$B$23,$A58,'S2'!$E$6:$E$23,"Ambos")+SUMIFS('S3'!$I$6:$I$19,'S3'!$B$6:$B$19,$A58,'S3'!$E$6:$E$19,"Víctor")+SUMIFS('S3'!$I$6:$I$19,'S3'!$B$6:$B$19,$A58,'S3'!$E$6:$E$19,"Ambos")+SUMIFS('S4'!$I$6:$I$20,'S4'!$B$6:$B$20,$A58,'S4'!$E$6:$E$20,"Víctor")+SUMIFS('S4'!$I$6:$I$20,'S4'!$B$6:$B$20,$A58,'S4'!$E$6:$E$20,"Ambos")+SUMIFS('S5'!$I$6:$I$20,'S5'!$B$6:$B$20,$A58,'S5'!$E$6:$E$20,"Víctor")+SUMIFS('S5'!$I$6:$I$20,'S5'!$B$6:$B$20,$A58,'S5'!$E$6:$E$20,"Ambos")+SUMIFS('S6'!$I$6:$I$17,'S6'!$B$6:$B$17,$A58,'S6'!$E$6:$E$17,"Víctor")+SUMIFS('S6'!$I$6:$I$17,'S6'!$B$6:$B$17,$A58,'S6'!$E$6:$E$17,"Ambos")+SUMIFS('S7'!$I$6:$I$19,'S7'!$B$6:$B$19,$A58,'S7'!$E$6:$E$19,"Víctor")+SUMIFS('S7'!$I$6:$I$19,'S7'!$B$6:$B$19,$A58,'S7'!$E$6:$E$19,"Ambos")+SUMIFS('S8'!$I$6:$I$23,'S8'!$B$6:$B$23,$A58,'S8'!$E$6:$E$23,"Víctor")+SUMIFS('S8'!$I$6:$I$23,'S8'!$B$6:$B$23,$A58,'S8'!$E$6:$E$23,"Ambos")+SUMIFS('S9'!$I$6:$I$15,'S9'!$B$6:$B$15,$A58,'S9'!$E$6:$E$15,"Víctor")+SUMIFS('S9'!$I$6:$I$15,'S9'!$B$6:$B$15,$A58,'S9'!$E$6:$E$15,"Ambos")+SUMIFS('S10'!$I$6:$I$13,'S10'!$B$6:$B$13,$A58,'S10'!$E$6:$E$13,"Víctor")+SUMIFS('S10'!$I$6:$I$13,'S10'!$B$6:$B$13,$A58,'S10'!$E$6:$E$13,"Ambos")+SUMIFS('Holgura'!$I$6:$I$11,'Holgura'!$B$6:$B$11,$A58,'Holgura'!$E$6:$E$11,"Víctor")+SUMIFS('Holgura'!$I$6:$I$11,'Holgura'!$B$6:$B$11,$A58,'Holgura'!$E$6:$E$11,"Ambos")+SUMIFS('Entrega'!$I$6:$I$9,'Entrega'!$B$6:$B$9,$A58,'Entrega'!$E$6:$E$9,"Víctor")+SUMIFS('Entrega'!$I$6:$I$9,'Entrega'!$B$6:$B$9,$A58,'Entrega'!$E$6:$E$9,"Ambos")+SUMIFS('Defensa'!$I$6:$I$10,'Defensa'!$B$6:$B$10,$A58,'Defensa'!$E$6:$E$10,"Víctor")+SUMIFS('Defensa'!$I$6:$I$10,'Defensa'!$B$6:$B$10,$A58,'Defensa'!$E$6:$E$10,"Ambos")</f>
+        <f>SUMIFS('S1'!$I$6:$I$32,'S1'!$B$6:$B$32,$A58,'S1'!$E$6:$E$32,"Víctor")+SUMIFS('S1'!$I$6:$I$32,'S1'!$B$6:$B$32,$A58,'S1'!$E$6:$E$32,"Ambos")+SUMIFS('S2'!$I$6:$I$23,'S2'!$B$6:$B$23,$A58,'S2'!$E$6:$E$23,"Víctor")+SUMIFS('S2'!$I$6:$I$23,'S2'!$B$6:$B$23,$A58,'S2'!$E$6:$E$23,"Ambos")+SUMIFS('S3'!$I$6:$I$24,'S3'!$B$6:$B$24,$A58,'S3'!$E$6:$E$24,"Víctor")+SUMIFS('S3'!$I$6:$I$24,'S3'!$B$6:$B$24,$A58,'S3'!$E$6:$E$24,"Ambos")+SUMIFS('S4'!$I$6:$I$22,'S4'!$B$6:$B$22,$A58,'S4'!$E$6:$E$22,"Víctor")+SUMIFS('S4'!$I$6:$I$22,'S4'!$B$6:$B$22,$A58,'S4'!$E$6:$E$22,"Ambos")+SUMIFS('S5'!$I$6:$I$20,'S5'!$B$6:$B$20,$A58,'S5'!$E$6:$E$20,"Víctor")+SUMIFS('S5'!$I$6:$I$20,'S5'!$B$6:$B$20,$A58,'S5'!$E$6:$E$20,"Ambos")+SUMIFS('S6'!$I$6:$I$17,'S6'!$B$6:$B$17,$A58,'S6'!$E$6:$E$17,"Víctor")+SUMIFS('S6'!$I$6:$I$17,'S6'!$B$6:$B$17,$A58,'S6'!$E$6:$E$17,"Ambos")+SUMIFS('S7'!$I$6:$I$19,'S7'!$B$6:$B$19,$A58,'S7'!$E$6:$E$19,"Víctor")+SUMIFS('S7'!$I$6:$I$19,'S7'!$B$6:$B$19,$A58,'S7'!$E$6:$E$19,"Ambos")+SUMIFS('S8'!$I$6:$I$23,'S8'!$B$6:$B$23,$A58,'S8'!$E$6:$E$23,"Víctor")+SUMIFS('S8'!$I$6:$I$23,'S8'!$B$6:$B$23,$A58,'S8'!$E$6:$E$23,"Ambos")+SUMIFS('S9'!$I$6:$I$15,'S9'!$B$6:$B$15,$A58,'S9'!$E$6:$E$15,"Víctor")+SUMIFS('S9'!$I$6:$I$15,'S9'!$B$6:$B$15,$A58,'S9'!$E$6:$E$15,"Ambos")+SUMIFS('S10'!$I$6:$I$13,'S10'!$B$6:$B$13,$A58,'S10'!$E$6:$E$13,"Víctor")+SUMIFS('S10'!$I$6:$I$13,'S10'!$B$6:$B$13,$A58,'S10'!$E$6:$E$13,"Ambos")+SUMIFS('Holgura'!$I$6:$I$11,'Holgura'!$B$6:$B$11,$A58,'Holgura'!$E$6:$E$11,"Víctor")+SUMIFS('Holgura'!$I$6:$I$11,'Holgura'!$B$6:$B$11,$A58,'Holgura'!$E$6:$E$11,"Ambos")+SUMIFS('Entrega'!$I$6:$I$9,'Entrega'!$B$6:$B$9,$A58,'Entrega'!$E$6:$E$9,"Víctor")+SUMIFS('Entrega'!$I$6:$I$9,'Entrega'!$B$6:$B$9,$A58,'Entrega'!$E$6:$E$9,"Ambos")+SUMIFS('Defensa'!$I$6:$I$10,'Defensa'!$B$6:$B$10,$A58,'Defensa'!$E$6:$E$10,"Víctor")+SUMIFS('Defensa'!$I$6:$I$10,'Defensa'!$B$6:$B$10,$A58,'Defensa'!$E$6:$E$10,"Ambos")</f>
         <v/>
       </c>
       <c r="E58" s="21">
-        <f>SUMIFS('S1'!$I$6:$I$32,'S1'!$B$6:$B$32,$A58,'S1'!$E$6:$E$32,"Diego")+SUMIFS('S1'!$I$6:$I$32,'S1'!$B$6:$B$32,$A58,'S1'!$E$6:$E$32,"Ambos")+SUMIFS('S2'!$I$6:$I$23,'S2'!$B$6:$B$23,$A58,'S2'!$E$6:$E$23,"Diego")+SUMIFS('S2'!$I$6:$I$23,'S2'!$B$6:$B$23,$A58,'S2'!$E$6:$E$23,"Ambos")+SUMIFS('S3'!$I$6:$I$19,'S3'!$B$6:$B$19,$A58,'S3'!$E$6:$E$19,"Diego")+SUMIFS('S3'!$I$6:$I$19,'S3'!$B$6:$B$19,$A58,'S3'!$E$6:$E$19,"Ambos")+SUMIFS('S4'!$I$6:$I$20,'S4'!$B$6:$B$20,$A58,'S4'!$E$6:$E$20,"Diego")+SUMIFS('S4'!$I$6:$I$20,'S4'!$B$6:$B$20,$A58,'S4'!$E$6:$E$20,"Ambos")+SUMIFS('S5'!$I$6:$I$20,'S5'!$B$6:$B$20,$A58,'S5'!$E$6:$E$20,"Diego")+SUMIFS('S5'!$I$6:$I$20,'S5'!$B$6:$B$20,$A58,'S5'!$E$6:$E$20,"Ambos")+SUMIFS('S6'!$I$6:$I$17,'S6'!$B$6:$B$17,$A58,'S6'!$E$6:$E$17,"Diego")+SUMIFS('S6'!$I$6:$I$17,'S6'!$B$6:$B$17,$A58,'S6'!$E$6:$E$17,"Ambos")+SUMIFS('S7'!$I$6:$I$19,'S7'!$B$6:$B$19,$A58,'S7'!$E$6:$E$19,"Diego")+SUMIFS('S7'!$I$6:$I$19,'S7'!$B$6:$B$19,$A58,'S7'!$E$6:$E$19,"Ambos")+SUMIFS('S8'!$I$6:$I$23,'S8'!$B$6:$B$23,$A58,'S8'!$E$6:$E$23,"Diego")+SUMIFS('S8'!$I$6:$I$23,'S8'!$B$6:$B$23,$A58,'S8'!$E$6:$E$23,"Ambos")+SUMIFS('S9'!$I$6:$I$15,'S9'!$B$6:$B$15,$A58,'S9'!$E$6:$E$15,"Diego")+SUMIFS('S9'!$I$6:$I$15,'S9'!$B$6:$B$15,$A58,'S9'!$E$6:$E$15,"Ambos")+SUMIFS('S10'!$I$6:$I$13,'S10'!$B$6:$B$13,$A58,'S10'!$E$6:$E$13,"Diego")+SUMIFS('S10'!$I$6:$I$13,'S10'!$B$6:$B$13,$A58,'S10'!$E$6:$E$13,"Ambos")+SUMIFS('Holgura'!$I$6:$I$11,'Holgura'!$B$6:$B$11,$A58,'Holgura'!$E$6:$E$11,"Diego")+SUMIFS('Holgura'!$I$6:$I$11,'Holgura'!$B$6:$B$11,$A58,'Holgura'!$E$6:$E$11,"Ambos")+SUMIFS('Entrega'!$I$6:$I$9,'Entrega'!$B$6:$B$9,$A58,'Entrega'!$E$6:$E$9,"Diego")+SUMIFS('Entrega'!$I$6:$I$9,'Entrega'!$B$6:$B$9,$A58,'Entrega'!$E$6:$E$9,"Ambos")+SUMIFS('Defensa'!$I$6:$I$10,'Defensa'!$B$6:$B$10,$A58,'Defensa'!$E$6:$E$10,"Diego")+SUMIFS('Defensa'!$I$6:$I$10,'Defensa'!$B$6:$B$10,$A58,'Defensa'!$E$6:$E$10,"Ambos")</f>
+        <f>SUMIFS('S1'!$I$6:$I$32,'S1'!$B$6:$B$32,$A58,'S1'!$E$6:$E$32,"Diego")+SUMIFS('S1'!$I$6:$I$32,'S1'!$B$6:$B$32,$A58,'S1'!$E$6:$E$32,"Ambos")+SUMIFS('S2'!$I$6:$I$23,'S2'!$B$6:$B$23,$A58,'S2'!$E$6:$E$23,"Diego")+SUMIFS('S2'!$I$6:$I$23,'S2'!$B$6:$B$23,$A58,'S2'!$E$6:$E$23,"Ambos")+SUMIFS('S3'!$I$6:$I$24,'S3'!$B$6:$B$24,$A58,'S3'!$E$6:$E$24,"Diego")+SUMIFS('S3'!$I$6:$I$24,'S3'!$B$6:$B$24,$A58,'S3'!$E$6:$E$24,"Ambos")+SUMIFS('S4'!$I$6:$I$22,'S4'!$B$6:$B$22,$A58,'S4'!$E$6:$E$22,"Diego")+SUMIFS('S4'!$I$6:$I$22,'S4'!$B$6:$B$22,$A58,'S4'!$E$6:$E$22,"Ambos")+SUMIFS('S5'!$I$6:$I$20,'S5'!$B$6:$B$20,$A58,'S5'!$E$6:$E$20,"Diego")+SUMIFS('S5'!$I$6:$I$20,'S5'!$B$6:$B$20,$A58,'S5'!$E$6:$E$20,"Ambos")+SUMIFS('S6'!$I$6:$I$17,'S6'!$B$6:$B$17,$A58,'S6'!$E$6:$E$17,"Diego")+SUMIFS('S6'!$I$6:$I$17,'S6'!$B$6:$B$17,$A58,'S6'!$E$6:$E$17,"Ambos")+SUMIFS('S7'!$I$6:$I$19,'S7'!$B$6:$B$19,$A58,'S7'!$E$6:$E$19,"Diego")+SUMIFS('S7'!$I$6:$I$19,'S7'!$B$6:$B$19,$A58,'S7'!$E$6:$E$19,"Ambos")+SUMIFS('S8'!$I$6:$I$23,'S8'!$B$6:$B$23,$A58,'S8'!$E$6:$E$23,"Diego")+SUMIFS('S8'!$I$6:$I$23,'S8'!$B$6:$B$23,$A58,'S8'!$E$6:$E$23,"Ambos")+SUMIFS('S9'!$I$6:$I$15,'S9'!$B$6:$B$15,$A58,'S9'!$E$6:$E$15,"Diego")+SUMIFS('S9'!$I$6:$I$15,'S9'!$B$6:$B$15,$A58,'S9'!$E$6:$E$15,"Ambos")+SUMIFS('S10'!$I$6:$I$13,'S10'!$B$6:$B$13,$A58,'S10'!$E$6:$E$13,"Diego")+SUMIFS('S10'!$I$6:$I$13,'S10'!$B$6:$B$13,$A58,'S10'!$E$6:$E$13,"Ambos")+SUMIFS('Holgura'!$I$6:$I$11,'Holgura'!$B$6:$B$11,$A58,'Holgura'!$E$6:$E$11,"Diego")+SUMIFS('Holgura'!$I$6:$I$11,'Holgura'!$B$6:$B$11,$A58,'Holgura'!$E$6:$E$11,"Ambos")+SUMIFS('Entrega'!$I$6:$I$9,'Entrega'!$B$6:$B$9,$A58,'Entrega'!$E$6:$E$9,"Diego")+SUMIFS('Entrega'!$I$6:$I$9,'Entrega'!$B$6:$B$9,$A58,'Entrega'!$E$6:$E$9,"Ambos")+SUMIFS('Defensa'!$I$6:$I$10,'Defensa'!$B$6:$B$10,$A58,'Defensa'!$E$6:$E$10,"Diego")+SUMIFS('Defensa'!$I$6:$I$10,'Defensa'!$B$6:$B$10,$A58,'Defensa'!$E$6:$E$10,"Ambos")</f>
         <v/>
       </c>
       <c r="F58" s="21">
-        <f>COUNTIFS('S1'!$B$6:$B$32,$A58,'S1'!$E$6:$E$32,"Víctor")+COUNTIFS('S1'!$B$6:$B$32,$A58,'S1'!$E$6:$E$32,"Ambos")+COUNTIFS('S2'!$B$6:$B$23,$A58,'S2'!$E$6:$E$23,"Víctor")+COUNTIFS('S2'!$B$6:$B$23,$A58,'S2'!$E$6:$E$23,"Ambos")+COUNTIFS('S3'!$B$6:$B$19,$A58,'S3'!$E$6:$E$19,"Víctor")+COUNTIFS('S3'!$B$6:$B$19,$A58,'S3'!$E$6:$E$19,"Ambos")+COUNTIFS('S4'!$B$6:$B$20,$A58,'S4'!$E$6:$E$20,"Víctor")+COUNTIFS('S4'!$B$6:$B$20,$A58,'S4'!$E$6:$E$20,"Ambos")+COUNTIFS('S5'!$B$6:$B$20,$A58,'S5'!$E$6:$E$20,"Víctor")+COUNTIFS('S5'!$B$6:$B$20,$A58,'S5'!$E$6:$E$20,"Ambos")+COUNTIFS('S6'!$B$6:$B$17,$A58,'S6'!$E$6:$E$17,"Víctor")+COUNTIFS('S6'!$B$6:$B$17,$A58,'S6'!$E$6:$E$17,"Ambos")+COUNTIFS('S7'!$B$6:$B$19,$A58,'S7'!$E$6:$E$19,"Víctor")+COUNTIFS('S7'!$B$6:$B$19,$A58,'S7'!$E$6:$E$19,"Ambos")+COUNTIFS('S8'!$B$6:$B$23,$A58,'S8'!$E$6:$E$23,"Víctor")+COUNTIFS('S8'!$B$6:$B$23,$A58,'S8'!$E$6:$E$23,"Ambos")+COUNTIFS('S9'!$B$6:$B$15,$A58,'S9'!$E$6:$E$15,"Víctor")+COUNTIFS('S9'!$B$6:$B$15,$A58,'S9'!$E$6:$E$15,"Ambos")+COUNTIFS('S10'!$B$6:$B$13,$A58,'S10'!$E$6:$E$13,"Víctor")+COUNTIFS('S10'!$B$6:$B$13,$A58,'S10'!$E$6:$E$13,"Ambos")+COUNTIFS('Holgura'!$B$6:$B$11,$A58,'Holgura'!$E$6:$E$11,"Víctor")+COUNTIFS('Holgura'!$B$6:$B$11,$A58,'Holgura'!$E$6:$E$11,"Ambos")+COUNTIFS('Entrega'!$B$6:$B$9,$A58,'Entrega'!$E$6:$E$9,"Víctor")+COUNTIFS('Entrega'!$B$6:$B$9,$A58,'Entrega'!$E$6:$E$9,"Ambos")+COUNTIFS('Defensa'!$B$6:$B$10,$A58,'Defensa'!$E$6:$E$10,"Víctor")+COUNTIFS('Defensa'!$B$6:$B$10,$A58,'Defensa'!$E$6:$E$10,"Ambos")</f>
+        <f>COUNTIFS('S1'!$B$6:$B$32,$A58,'S1'!$E$6:$E$32,"Víctor")+COUNTIFS('S1'!$B$6:$B$32,$A58,'S1'!$E$6:$E$32,"Ambos")+COUNTIFS('S2'!$B$6:$B$23,$A58,'S2'!$E$6:$E$23,"Víctor")+COUNTIFS('S2'!$B$6:$B$23,$A58,'S2'!$E$6:$E$23,"Ambos")+COUNTIFS('S3'!$B$6:$B$24,$A58,'S3'!$E$6:$E$24,"Víctor")+COUNTIFS('S3'!$B$6:$B$24,$A58,'S3'!$E$6:$E$24,"Ambos")+COUNTIFS('S4'!$B$6:$B$22,$A58,'S4'!$E$6:$E$22,"Víctor")+COUNTIFS('S4'!$B$6:$B$22,$A58,'S4'!$E$6:$E$22,"Ambos")+COUNTIFS('S5'!$B$6:$B$20,$A58,'S5'!$E$6:$E$20,"Víctor")+COUNTIFS('S5'!$B$6:$B$20,$A58,'S5'!$E$6:$E$20,"Ambos")+COUNTIFS('S6'!$B$6:$B$17,$A58,'S6'!$E$6:$E$17,"Víctor")+COUNTIFS('S6'!$B$6:$B$17,$A58,'S6'!$E$6:$E$17,"Ambos")+COUNTIFS('S7'!$B$6:$B$19,$A58,'S7'!$E$6:$E$19,"Víctor")+COUNTIFS('S7'!$B$6:$B$19,$A58,'S7'!$E$6:$E$19,"Ambos")+COUNTIFS('S8'!$B$6:$B$23,$A58,'S8'!$E$6:$E$23,"Víctor")+COUNTIFS('S8'!$B$6:$B$23,$A58,'S8'!$E$6:$E$23,"Ambos")+COUNTIFS('S9'!$B$6:$B$15,$A58,'S9'!$E$6:$E$15,"Víctor")+COUNTIFS('S9'!$B$6:$B$15,$A58,'S9'!$E$6:$E$15,"Ambos")+COUNTIFS('S10'!$B$6:$B$13,$A58,'S10'!$E$6:$E$13,"Víctor")+COUNTIFS('S10'!$B$6:$B$13,$A58,'S10'!$E$6:$E$13,"Ambos")+COUNTIFS('Holgura'!$B$6:$B$11,$A58,'Holgura'!$E$6:$E$11,"Víctor")+COUNTIFS('Holgura'!$B$6:$B$11,$A58,'Holgura'!$E$6:$E$11,"Ambos")+COUNTIFS('Entrega'!$B$6:$B$9,$A58,'Entrega'!$E$6:$E$9,"Víctor")+COUNTIFS('Entrega'!$B$6:$B$9,$A58,'Entrega'!$E$6:$E$9,"Ambos")+COUNTIFS('Defensa'!$B$6:$B$10,$A58,'Defensa'!$E$6:$E$10,"Víctor")+COUNTIFS('Defensa'!$B$6:$B$10,$A58,'Defensa'!$E$6:$E$10,"Ambos")</f>
         <v/>
       </c>
       <c r="G58" s="21">
-        <f>COUNTIFS('S1'!$B$6:$B$32,$A58,'S1'!$E$6:$E$32,"Diego")+COUNTIFS('S1'!$B$6:$B$32,$A58,'S1'!$E$6:$E$32,"Ambos")+COUNTIFS('S2'!$B$6:$B$23,$A58,'S2'!$E$6:$E$23,"Diego")+COUNTIFS('S2'!$B$6:$B$23,$A58,'S2'!$E$6:$E$23,"Ambos")+COUNTIFS('S3'!$B$6:$B$19,$A58,'S3'!$E$6:$E$19,"Diego")+COUNTIFS('S3'!$B$6:$B$19,$A58,'S3'!$E$6:$E$19,"Ambos")+COUNTIFS('S4'!$B$6:$B$20,$A58,'S4'!$E$6:$E$20,"Diego")+COUNTIFS('S4'!$B$6:$B$20,$A58,'S4'!$E$6:$E$20,"Ambos")+COUNTIFS('S5'!$B$6:$B$20,$A58,'S5'!$E$6:$E$20,"Diego")+COUNTIFS('S5'!$B$6:$B$20,$A58,'S5'!$E$6:$E$20,"Ambos")+COUNTIFS('S6'!$B$6:$B$17,$A58,'S6'!$E$6:$E$17,"Diego")+COUNTIFS('S6'!$B$6:$B$17,$A58,'S6'!$E$6:$E$17,"Ambos")+COUNTIFS('S7'!$B$6:$B$19,$A58,'S7'!$E$6:$E$19,"Diego")+COUNTIFS('S7'!$B$6:$B$19,$A58,'S7'!$E$6:$E$19,"Ambos")+COUNTIFS('S8'!$B$6:$B$23,$A58,'S8'!$E$6:$E$23,"Diego")+COUNTIFS('S8'!$B$6:$B$23,$A58,'S8'!$E$6:$E$23,"Ambos")+COUNTIFS('S9'!$B$6:$B$15,$A58,'S9'!$E$6:$E$15,"Diego")+COUNTIFS('S9'!$B$6:$B$15,$A58,'S9'!$E$6:$E$15,"Ambos")+COUNTIFS('S10'!$B$6:$B$13,$A58,'S10'!$E$6:$E$13,"Diego")+COUNTIFS('S10'!$B$6:$B$13,$A58,'S10'!$E$6:$E$13,"Ambos")+COUNTIFS('Holgura'!$B$6:$B$11,$A58,'Holgura'!$E$6:$E$11,"Diego")+COUNTIFS('Holgura'!$B$6:$B$11,$A58,'Holgura'!$E$6:$E$11,"Ambos")+COUNTIFS('Entrega'!$B$6:$B$9,$A58,'Entrega'!$E$6:$E$9,"Diego")+COUNTIFS('Entrega'!$B$6:$B$9,$A58,'Entrega'!$E$6:$E$9,"Ambos")+COUNTIFS('Defensa'!$B$6:$B$10,$A58,'Defensa'!$E$6:$E$10,"Diego")+COUNTIFS('Defensa'!$B$6:$B$10,$A58,'Defensa'!$E$6:$E$10,"Ambos")</f>
+        <f>COUNTIFS('S1'!$B$6:$B$32,$A58,'S1'!$E$6:$E$32,"Diego")+COUNTIFS('S1'!$B$6:$B$32,$A58,'S1'!$E$6:$E$32,"Ambos")+COUNTIFS('S2'!$B$6:$B$23,$A58,'S2'!$E$6:$E$23,"Diego")+COUNTIFS('S2'!$B$6:$B$23,$A58,'S2'!$E$6:$E$23,"Ambos")+COUNTIFS('S3'!$B$6:$B$24,$A58,'S3'!$E$6:$E$24,"Diego")+COUNTIFS('S3'!$B$6:$B$24,$A58,'S3'!$E$6:$E$24,"Ambos")+COUNTIFS('S4'!$B$6:$B$22,$A58,'S4'!$E$6:$E$22,"Diego")+COUNTIFS('S4'!$B$6:$B$22,$A58,'S4'!$E$6:$E$22,"Ambos")+COUNTIFS('S5'!$B$6:$B$20,$A58,'S5'!$E$6:$E$20,"Diego")+COUNTIFS('S5'!$B$6:$B$20,$A58,'S5'!$E$6:$E$20,"Ambos")+COUNTIFS('S6'!$B$6:$B$17,$A58,'S6'!$E$6:$E$17,"Diego")+COUNTIFS('S6'!$B$6:$B$17,$A58,'S6'!$E$6:$E$17,"Ambos")+COUNTIFS('S7'!$B$6:$B$19,$A58,'S7'!$E$6:$E$19,"Diego")+COUNTIFS('S7'!$B$6:$B$19,$A58,'S7'!$E$6:$E$19,"Ambos")+COUNTIFS('S8'!$B$6:$B$23,$A58,'S8'!$E$6:$E$23,"Diego")+COUNTIFS('S8'!$B$6:$B$23,$A58,'S8'!$E$6:$E$23,"Ambos")+COUNTIFS('S9'!$B$6:$B$15,$A58,'S9'!$E$6:$E$15,"Diego")+COUNTIFS('S9'!$B$6:$B$15,$A58,'S9'!$E$6:$E$15,"Ambos")+COUNTIFS('S10'!$B$6:$B$13,$A58,'S10'!$E$6:$E$13,"Diego")+COUNTIFS('S10'!$B$6:$B$13,$A58,'S10'!$E$6:$E$13,"Ambos")+COUNTIFS('Holgura'!$B$6:$B$11,$A58,'Holgura'!$E$6:$E$11,"Diego")+COUNTIFS('Holgura'!$B$6:$B$11,$A58,'Holgura'!$E$6:$E$11,"Ambos")+COUNTIFS('Entrega'!$B$6:$B$9,$A58,'Entrega'!$E$6:$E$9,"Diego")+COUNTIFS('Entrega'!$B$6:$B$9,$A58,'Entrega'!$E$6:$E$9,"Ambos")+COUNTIFS('Defensa'!$B$6:$B$10,$A58,'Defensa'!$E$6:$E$10,"Diego")+COUNTIFS('Defensa'!$B$6:$B$10,$A58,'Defensa'!$E$6:$E$10,"Ambos")</f>
         <v/>
       </c>
     </row>
@@ -10246,19 +10267,19 @@
         <v/>
       </c>
       <c r="D59" s="21">
-        <f>SUMIFS('S1'!$I$6:$I$32,'S1'!$B$6:$B$32,$A59,'S1'!$E$6:$E$32,"Víctor")+SUMIFS('S1'!$I$6:$I$32,'S1'!$B$6:$B$32,$A59,'S1'!$E$6:$E$32,"Ambos")+SUMIFS('S2'!$I$6:$I$23,'S2'!$B$6:$B$23,$A59,'S2'!$E$6:$E$23,"Víctor")+SUMIFS('S2'!$I$6:$I$23,'S2'!$B$6:$B$23,$A59,'S2'!$E$6:$E$23,"Ambos")+SUMIFS('S3'!$I$6:$I$19,'S3'!$B$6:$B$19,$A59,'S3'!$E$6:$E$19,"Víctor")+SUMIFS('S3'!$I$6:$I$19,'S3'!$B$6:$B$19,$A59,'S3'!$E$6:$E$19,"Ambos")+SUMIFS('S4'!$I$6:$I$20,'S4'!$B$6:$B$20,$A59,'S4'!$E$6:$E$20,"Víctor")+SUMIFS('S4'!$I$6:$I$20,'S4'!$B$6:$B$20,$A59,'S4'!$E$6:$E$20,"Ambos")+SUMIFS('S5'!$I$6:$I$20,'S5'!$B$6:$B$20,$A59,'S5'!$E$6:$E$20,"Víctor")+SUMIFS('S5'!$I$6:$I$20,'S5'!$B$6:$B$20,$A59,'S5'!$E$6:$E$20,"Ambos")+SUMIFS('S6'!$I$6:$I$17,'S6'!$B$6:$B$17,$A59,'S6'!$E$6:$E$17,"Víctor")+SUMIFS('S6'!$I$6:$I$17,'S6'!$B$6:$B$17,$A59,'S6'!$E$6:$E$17,"Ambos")+SUMIFS('S7'!$I$6:$I$19,'S7'!$B$6:$B$19,$A59,'S7'!$E$6:$E$19,"Víctor")+SUMIFS('S7'!$I$6:$I$19,'S7'!$B$6:$B$19,$A59,'S7'!$E$6:$E$19,"Ambos")+SUMIFS('S8'!$I$6:$I$23,'S8'!$B$6:$B$23,$A59,'S8'!$E$6:$E$23,"Víctor")+SUMIFS('S8'!$I$6:$I$23,'S8'!$B$6:$B$23,$A59,'S8'!$E$6:$E$23,"Ambos")+SUMIFS('S9'!$I$6:$I$15,'S9'!$B$6:$B$15,$A59,'S9'!$E$6:$E$15,"Víctor")+SUMIFS('S9'!$I$6:$I$15,'S9'!$B$6:$B$15,$A59,'S9'!$E$6:$E$15,"Ambos")+SUMIFS('S10'!$I$6:$I$13,'S10'!$B$6:$B$13,$A59,'S10'!$E$6:$E$13,"Víctor")+SUMIFS('S10'!$I$6:$I$13,'S10'!$B$6:$B$13,$A59,'S10'!$E$6:$E$13,"Ambos")+SUMIFS('Holgura'!$I$6:$I$11,'Holgura'!$B$6:$B$11,$A59,'Holgura'!$E$6:$E$11,"Víctor")+SUMIFS('Holgura'!$I$6:$I$11,'Holgura'!$B$6:$B$11,$A59,'Holgura'!$E$6:$E$11,"Ambos")+SUMIFS('Entrega'!$I$6:$I$9,'Entrega'!$B$6:$B$9,$A59,'Entrega'!$E$6:$E$9,"Víctor")+SUMIFS('Entrega'!$I$6:$I$9,'Entrega'!$B$6:$B$9,$A59,'Entrega'!$E$6:$E$9,"Ambos")+SUMIFS('Defensa'!$I$6:$I$10,'Defensa'!$B$6:$B$10,$A59,'Defensa'!$E$6:$E$10,"Víctor")+SUMIFS('Defensa'!$I$6:$I$10,'Defensa'!$B$6:$B$10,$A59,'Defensa'!$E$6:$E$10,"Ambos")</f>
+        <f>SUMIFS('S1'!$I$6:$I$32,'S1'!$B$6:$B$32,$A59,'S1'!$E$6:$E$32,"Víctor")+SUMIFS('S1'!$I$6:$I$32,'S1'!$B$6:$B$32,$A59,'S1'!$E$6:$E$32,"Ambos")+SUMIFS('S2'!$I$6:$I$23,'S2'!$B$6:$B$23,$A59,'S2'!$E$6:$E$23,"Víctor")+SUMIFS('S2'!$I$6:$I$23,'S2'!$B$6:$B$23,$A59,'S2'!$E$6:$E$23,"Ambos")+SUMIFS('S3'!$I$6:$I$24,'S3'!$B$6:$B$24,$A59,'S3'!$E$6:$E$24,"Víctor")+SUMIFS('S3'!$I$6:$I$24,'S3'!$B$6:$B$24,$A59,'S3'!$E$6:$E$24,"Ambos")+SUMIFS('S4'!$I$6:$I$22,'S4'!$B$6:$B$22,$A59,'S4'!$E$6:$E$22,"Víctor")+SUMIFS('S4'!$I$6:$I$22,'S4'!$B$6:$B$22,$A59,'S4'!$E$6:$E$22,"Ambos")+SUMIFS('S5'!$I$6:$I$20,'S5'!$B$6:$B$20,$A59,'S5'!$E$6:$E$20,"Víctor")+SUMIFS('S5'!$I$6:$I$20,'S5'!$B$6:$B$20,$A59,'S5'!$E$6:$E$20,"Ambos")+SUMIFS('S6'!$I$6:$I$17,'S6'!$B$6:$B$17,$A59,'S6'!$E$6:$E$17,"Víctor")+SUMIFS('S6'!$I$6:$I$17,'S6'!$B$6:$B$17,$A59,'S6'!$E$6:$E$17,"Ambos")+SUMIFS('S7'!$I$6:$I$19,'S7'!$B$6:$B$19,$A59,'S7'!$E$6:$E$19,"Víctor")+SUMIFS('S7'!$I$6:$I$19,'S7'!$B$6:$B$19,$A59,'S7'!$E$6:$E$19,"Ambos")+SUMIFS('S8'!$I$6:$I$23,'S8'!$B$6:$B$23,$A59,'S8'!$E$6:$E$23,"Víctor")+SUMIFS('S8'!$I$6:$I$23,'S8'!$B$6:$B$23,$A59,'S8'!$E$6:$E$23,"Ambos")+SUMIFS('S9'!$I$6:$I$15,'S9'!$B$6:$B$15,$A59,'S9'!$E$6:$E$15,"Víctor")+SUMIFS('S9'!$I$6:$I$15,'S9'!$B$6:$B$15,$A59,'S9'!$E$6:$E$15,"Ambos")+SUMIFS('S10'!$I$6:$I$13,'S10'!$B$6:$B$13,$A59,'S10'!$E$6:$E$13,"Víctor")+SUMIFS('S10'!$I$6:$I$13,'S10'!$B$6:$B$13,$A59,'S10'!$E$6:$E$13,"Ambos")+SUMIFS('Holgura'!$I$6:$I$11,'Holgura'!$B$6:$B$11,$A59,'Holgura'!$E$6:$E$11,"Víctor")+SUMIFS('Holgura'!$I$6:$I$11,'Holgura'!$B$6:$B$11,$A59,'Holgura'!$E$6:$E$11,"Ambos")+SUMIFS('Entrega'!$I$6:$I$9,'Entrega'!$B$6:$B$9,$A59,'Entrega'!$E$6:$E$9,"Víctor")+SUMIFS('Entrega'!$I$6:$I$9,'Entrega'!$B$6:$B$9,$A59,'Entrega'!$E$6:$E$9,"Ambos")+SUMIFS('Defensa'!$I$6:$I$10,'Defensa'!$B$6:$B$10,$A59,'Defensa'!$E$6:$E$10,"Víctor")+SUMIFS('Defensa'!$I$6:$I$10,'Defensa'!$B$6:$B$10,$A59,'Defensa'!$E$6:$E$10,"Ambos")</f>
         <v/>
       </c>
       <c r="E59" s="21">
-        <f>SUMIFS('S1'!$I$6:$I$32,'S1'!$B$6:$B$32,$A59,'S1'!$E$6:$E$32,"Diego")+SUMIFS('S1'!$I$6:$I$32,'S1'!$B$6:$B$32,$A59,'S1'!$E$6:$E$32,"Ambos")+SUMIFS('S2'!$I$6:$I$23,'S2'!$B$6:$B$23,$A59,'S2'!$E$6:$E$23,"Diego")+SUMIFS('S2'!$I$6:$I$23,'S2'!$B$6:$B$23,$A59,'S2'!$E$6:$E$23,"Ambos")+SUMIFS('S3'!$I$6:$I$19,'S3'!$B$6:$B$19,$A59,'S3'!$E$6:$E$19,"Diego")+SUMIFS('S3'!$I$6:$I$19,'S3'!$B$6:$B$19,$A59,'S3'!$E$6:$E$19,"Ambos")+SUMIFS('S4'!$I$6:$I$20,'S4'!$B$6:$B$20,$A59,'S4'!$E$6:$E$20,"Diego")+SUMIFS('S4'!$I$6:$I$20,'S4'!$B$6:$B$20,$A59,'S4'!$E$6:$E$20,"Ambos")+SUMIFS('S5'!$I$6:$I$20,'S5'!$B$6:$B$20,$A59,'S5'!$E$6:$E$20,"Diego")+SUMIFS('S5'!$I$6:$I$20,'S5'!$B$6:$B$20,$A59,'S5'!$E$6:$E$20,"Ambos")+SUMIFS('S6'!$I$6:$I$17,'S6'!$B$6:$B$17,$A59,'S6'!$E$6:$E$17,"Diego")+SUMIFS('S6'!$I$6:$I$17,'S6'!$B$6:$B$17,$A59,'S6'!$E$6:$E$17,"Ambos")+SUMIFS('S7'!$I$6:$I$19,'S7'!$B$6:$B$19,$A59,'S7'!$E$6:$E$19,"Diego")+SUMIFS('S7'!$I$6:$I$19,'S7'!$B$6:$B$19,$A59,'S7'!$E$6:$E$19,"Ambos")+SUMIFS('S8'!$I$6:$I$23,'S8'!$B$6:$B$23,$A59,'S8'!$E$6:$E$23,"Diego")+SUMIFS('S8'!$I$6:$I$23,'S8'!$B$6:$B$23,$A59,'S8'!$E$6:$E$23,"Ambos")+SUMIFS('S9'!$I$6:$I$15,'S9'!$B$6:$B$15,$A59,'S9'!$E$6:$E$15,"Diego")+SUMIFS('S9'!$I$6:$I$15,'S9'!$B$6:$B$15,$A59,'S9'!$E$6:$E$15,"Ambos")+SUMIFS('S10'!$I$6:$I$13,'S10'!$B$6:$B$13,$A59,'S10'!$E$6:$E$13,"Diego")+SUMIFS('S10'!$I$6:$I$13,'S10'!$B$6:$B$13,$A59,'S10'!$E$6:$E$13,"Ambos")+SUMIFS('Holgura'!$I$6:$I$11,'Holgura'!$B$6:$B$11,$A59,'Holgura'!$E$6:$E$11,"Diego")+SUMIFS('Holgura'!$I$6:$I$11,'Holgura'!$B$6:$B$11,$A59,'Holgura'!$E$6:$E$11,"Ambos")+SUMIFS('Entrega'!$I$6:$I$9,'Entrega'!$B$6:$B$9,$A59,'Entrega'!$E$6:$E$9,"Diego")+SUMIFS('Entrega'!$I$6:$I$9,'Entrega'!$B$6:$B$9,$A59,'Entrega'!$E$6:$E$9,"Ambos")+SUMIFS('Defensa'!$I$6:$I$10,'Defensa'!$B$6:$B$10,$A59,'Defensa'!$E$6:$E$10,"Diego")+SUMIFS('Defensa'!$I$6:$I$10,'Defensa'!$B$6:$B$10,$A59,'Defensa'!$E$6:$E$10,"Ambos")</f>
+        <f>SUMIFS('S1'!$I$6:$I$32,'S1'!$B$6:$B$32,$A59,'S1'!$E$6:$E$32,"Diego")+SUMIFS('S1'!$I$6:$I$32,'S1'!$B$6:$B$32,$A59,'S1'!$E$6:$E$32,"Ambos")+SUMIFS('S2'!$I$6:$I$23,'S2'!$B$6:$B$23,$A59,'S2'!$E$6:$E$23,"Diego")+SUMIFS('S2'!$I$6:$I$23,'S2'!$B$6:$B$23,$A59,'S2'!$E$6:$E$23,"Ambos")+SUMIFS('S3'!$I$6:$I$24,'S3'!$B$6:$B$24,$A59,'S3'!$E$6:$E$24,"Diego")+SUMIFS('S3'!$I$6:$I$24,'S3'!$B$6:$B$24,$A59,'S3'!$E$6:$E$24,"Ambos")+SUMIFS('S4'!$I$6:$I$22,'S4'!$B$6:$B$22,$A59,'S4'!$E$6:$E$22,"Diego")+SUMIFS('S4'!$I$6:$I$22,'S4'!$B$6:$B$22,$A59,'S4'!$E$6:$E$22,"Ambos")+SUMIFS('S5'!$I$6:$I$20,'S5'!$B$6:$B$20,$A59,'S5'!$E$6:$E$20,"Diego")+SUMIFS('S5'!$I$6:$I$20,'S5'!$B$6:$B$20,$A59,'S5'!$E$6:$E$20,"Ambos")+SUMIFS('S6'!$I$6:$I$17,'S6'!$B$6:$B$17,$A59,'S6'!$E$6:$E$17,"Diego")+SUMIFS('S6'!$I$6:$I$17,'S6'!$B$6:$B$17,$A59,'S6'!$E$6:$E$17,"Ambos")+SUMIFS('S7'!$I$6:$I$19,'S7'!$B$6:$B$19,$A59,'S7'!$E$6:$E$19,"Diego")+SUMIFS('S7'!$I$6:$I$19,'S7'!$B$6:$B$19,$A59,'S7'!$E$6:$E$19,"Ambos")+SUMIFS('S8'!$I$6:$I$23,'S8'!$B$6:$B$23,$A59,'S8'!$E$6:$E$23,"Diego")+SUMIFS('S8'!$I$6:$I$23,'S8'!$B$6:$B$23,$A59,'S8'!$E$6:$E$23,"Ambos")+SUMIFS('S9'!$I$6:$I$15,'S9'!$B$6:$B$15,$A59,'S9'!$E$6:$E$15,"Diego")+SUMIFS('S9'!$I$6:$I$15,'S9'!$B$6:$B$15,$A59,'S9'!$E$6:$E$15,"Ambos")+SUMIFS('S10'!$I$6:$I$13,'S10'!$B$6:$B$13,$A59,'S10'!$E$6:$E$13,"Diego")+SUMIFS('S10'!$I$6:$I$13,'S10'!$B$6:$B$13,$A59,'S10'!$E$6:$E$13,"Ambos")+SUMIFS('Holgura'!$I$6:$I$11,'Holgura'!$B$6:$B$11,$A59,'Holgura'!$E$6:$E$11,"Diego")+SUMIFS('Holgura'!$I$6:$I$11,'Holgura'!$B$6:$B$11,$A59,'Holgura'!$E$6:$E$11,"Ambos")+SUMIFS('Entrega'!$I$6:$I$9,'Entrega'!$B$6:$B$9,$A59,'Entrega'!$E$6:$E$9,"Diego")+SUMIFS('Entrega'!$I$6:$I$9,'Entrega'!$B$6:$B$9,$A59,'Entrega'!$E$6:$E$9,"Ambos")+SUMIFS('Defensa'!$I$6:$I$10,'Defensa'!$B$6:$B$10,$A59,'Defensa'!$E$6:$E$10,"Diego")+SUMIFS('Defensa'!$I$6:$I$10,'Defensa'!$B$6:$B$10,$A59,'Defensa'!$E$6:$E$10,"Ambos")</f>
         <v/>
       </c>
       <c r="F59" s="21">
-        <f>COUNTIFS('S1'!$B$6:$B$32,$A59,'S1'!$E$6:$E$32,"Víctor")+COUNTIFS('S1'!$B$6:$B$32,$A59,'S1'!$E$6:$E$32,"Ambos")+COUNTIFS('S2'!$B$6:$B$23,$A59,'S2'!$E$6:$E$23,"Víctor")+COUNTIFS('S2'!$B$6:$B$23,$A59,'S2'!$E$6:$E$23,"Ambos")+COUNTIFS('S3'!$B$6:$B$19,$A59,'S3'!$E$6:$E$19,"Víctor")+COUNTIFS('S3'!$B$6:$B$19,$A59,'S3'!$E$6:$E$19,"Ambos")+COUNTIFS('S4'!$B$6:$B$20,$A59,'S4'!$E$6:$E$20,"Víctor")+COUNTIFS('S4'!$B$6:$B$20,$A59,'S4'!$E$6:$E$20,"Ambos")+COUNTIFS('S5'!$B$6:$B$20,$A59,'S5'!$E$6:$E$20,"Víctor")+COUNTIFS('S5'!$B$6:$B$20,$A59,'S5'!$E$6:$E$20,"Ambos")+COUNTIFS('S6'!$B$6:$B$17,$A59,'S6'!$E$6:$E$17,"Víctor")+COUNTIFS('S6'!$B$6:$B$17,$A59,'S6'!$E$6:$E$17,"Ambos")+COUNTIFS('S7'!$B$6:$B$19,$A59,'S7'!$E$6:$E$19,"Víctor")+COUNTIFS('S7'!$B$6:$B$19,$A59,'S7'!$E$6:$E$19,"Ambos")+COUNTIFS('S8'!$B$6:$B$23,$A59,'S8'!$E$6:$E$23,"Víctor")+COUNTIFS('S8'!$B$6:$B$23,$A59,'S8'!$E$6:$E$23,"Ambos")+COUNTIFS('S9'!$B$6:$B$15,$A59,'S9'!$E$6:$E$15,"Víctor")+COUNTIFS('S9'!$B$6:$B$15,$A59,'S9'!$E$6:$E$15,"Ambos")+COUNTIFS('S10'!$B$6:$B$13,$A59,'S10'!$E$6:$E$13,"Víctor")+COUNTIFS('S10'!$B$6:$B$13,$A59,'S10'!$E$6:$E$13,"Ambos")+COUNTIFS('Holgura'!$B$6:$B$11,$A59,'Holgura'!$E$6:$E$11,"Víctor")+COUNTIFS('Holgura'!$B$6:$B$11,$A59,'Holgura'!$E$6:$E$11,"Ambos")+COUNTIFS('Entrega'!$B$6:$B$9,$A59,'Entrega'!$E$6:$E$9,"Víctor")+COUNTIFS('Entrega'!$B$6:$B$9,$A59,'Entrega'!$E$6:$E$9,"Ambos")+COUNTIFS('Defensa'!$B$6:$B$10,$A59,'Defensa'!$E$6:$E$10,"Víctor")+COUNTIFS('Defensa'!$B$6:$B$10,$A59,'Defensa'!$E$6:$E$10,"Ambos")</f>
+        <f>COUNTIFS('S1'!$B$6:$B$32,$A59,'S1'!$E$6:$E$32,"Víctor")+COUNTIFS('S1'!$B$6:$B$32,$A59,'S1'!$E$6:$E$32,"Ambos")+COUNTIFS('S2'!$B$6:$B$23,$A59,'S2'!$E$6:$E$23,"Víctor")+COUNTIFS('S2'!$B$6:$B$23,$A59,'S2'!$E$6:$E$23,"Ambos")+COUNTIFS('S3'!$B$6:$B$24,$A59,'S3'!$E$6:$E$24,"Víctor")+COUNTIFS('S3'!$B$6:$B$24,$A59,'S3'!$E$6:$E$24,"Ambos")+COUNTIFS('S4'!$B$6:$B$22,$A59,'S4'!$E$6:$E$22,"Víctor")+COUNTIFS('S4'!$B$6:$B$22,$A59,'S4'!$E$6:$E$22,"Ambos")+COUNTIFS('S5'!$B$6:$B$20,$A59,'S5'!$E$6:$E$20,"Víctor")+COUNTIFS('S5'!$B$6:$B$20,$A59,'S5'!$E$6:$E$20,"Ambos")+COUNTIFS('S6'!$B$6:$B$17,$A59,'S6'!$E$6:$E$17,"Víctor")+COUNTIFS('S6'!$B$6:$B$17,$A59,'S6'!$E$6:$E$17,"Ambos")+COUNTIFS('S7'!$B$6:$B$19,$A59,'S7'!$E$6:$E$19,"Víctor")+COUNTIFS('S7'!$B$6:$B$19,$A59,'S7'!$E$6:$E$19,"Ambos")+COUNTIFS('S8'!$B$6:$B$23,$A59,'S8'!$E$6:$E$23,"Víctor")+COUNTIFS('S8'!$B$6:$B$23,$A59,'S8'!$E$6:$E$23,"Ambos")+COUNTIFS('S9'!$B$6:$B$15,$A59,'S9'!$E$6:$E$15,"Víctor")+COUNTIFS('S9'!$B$6:$B$15,$A59,'S9'!$E$6:$E$15,"Ambos")+COUNTIFS('S10'!$B$6:$B$13,$A59,'S10'!$E$6:$E$13,"Víctor")+COUNTIFS('S10'!$B$6:$B$13,$A59,'S10'!$E$6:$E$13,"Ambos")+COUNTIFS('Holgura'!$B$6:$B$11,$A59,'Holgura'!$E$6:$E$11,"Víctor")+COUNTIFS('Holgura'!$B$6:$B$11,$A59,'Holgura'!$E$6:$E$11,"Ambos")+COUNTIFS('Entrega'!$B$6:$B$9,$A59,'Entrega'!$E$6:$E$9,"Víctor")+COUNTIFS('Entrega'!$B$6:$B$9,$A59,'Entrega'!$E$6:$E$9,"Ambos")+COUNTIFS('Defensa'!$B$6:$B$10,$A59,'Defensa'!$E$6:$E$10,"Víctor")+COUNTIFS('Defensa'!$B$6:$B$10,$A59,'Defensa'!$E$6:$E$10,"Ambos")</f>
         <v/>
       </c>
       <c r="G59" s="21">
-        <f>COUNTIFS('S1'!$B$6:$B$32,$A59,'S1'!$E$6:$E$32,"Diego")+COUNTIFS('S1'!$B$6:$B$32,$A59,'S1'!$E$6:$E$32,"Ambos")+COUNTIFS('S2'!$B$6:$B$23,$A59,'S2'!$E$6:$E$23,"Diego")+COUNTIFS('S2'!$B$6:$B$23,$A59,'S2'!$E$6:$E$23,"Ambos")+COUNTIFS('S3'!$B$6:$B$19,$A59,'S3'!$E$6:$E$19,"Diego")+COUNTIFS('S3'!$B$6:$B$19,$A59,'S3'!$E$6:$E$19,"Ambos")+COUNTIFS('S4'!$B$6:$B$20,$A59,'S4'!$E$6:$E$20,"Diego")+COUNTIFS('S4'!$B$6:$B$20,$A59,'S4'!$E$6:$E$20,"Ambos")+COUNTIFS('S5'!$B$6:$B$20,$A59,'S5'!$E$6:$E$20,"Diego")+COUNTIFS('S5'!$B$6:$B$20,$A59,'S5'!$E$6:$E$20,"Ambos")+COUNTIFS('S6'!$B$6:$B$17,$A59,'S6'!$E$6:$E$17,"Diego")+COUNTIFS('S6'!$B$6:$B$17,$A59,'S6'!$E$6:$E$17,"Ambos")+COUNTIFS('S7'!$B$6:$B$19,$A59,'S7'!$E$6:$E$19,"Diego")+COUNTIFS('S7'!$B$6:$B$19,$A59,'S7'!$E$6:$E$19,"Ambos")+COUNTIFS('S8'!$B$6:$B$23,$A59,'S8'!$E$6:$E$23,"Diego")+COUNTIFS('S8'!$B$6:$B$23,$A59,'S8'!$E$6:$E$23,"Ambos")+COUNTIFS('S9'!$B$6:$B$15,$A59,'S9'!$E$6:$E$15,"Diego")+COUNTIFS('S9'!$B$6:$B$15,$A59,'S9'!$E$6:$E$15,"Ambos")+COUNTIFS('S10'!$B$6:$B$13,$A59,'S10'!$E$6:$E$13,"Diego")+COUNTIFS('S10'!$B$6:$B$13,$A59,'S10'!$E$6:$E$13,"Ambos")+COUNTIFS('Holgura'!$B$6:$B$11,$A59,'Holgura'!$E$6:$E$11,"Diego")+COUNTIFS('Holgura'!$B$6:$B$11,$A59,'Holgura'!$E$6:$E$11,"Ambos")+COUNTIFS('Entrega'!$B$6:$B$9,$A59,'Entrega'!$E$6:$E$9,"Diego")+COUNTIFS('Entrega'!$B$6:$B$9,$A59,'Entrega'!$E$6:$E$9,"Ambos")+COUNTIFS('Defensa'!$B$6:$B$10,$A59,'Defensa'!$E$6:$E$10,"Diego")+COUNTIFS('Defensa'!$B$6:$B$10,$A59,'Defensa'!$E$6:$E$10,"Ambos")</f>
+        <f>COUNTIFS('S1'!$B$6:$B$32,$A59,'S1'!$E$6:$E$32,"Diego")+COUNTIFS('S1'!$B$6:$B$32,$A59,'S1'!$E$6:$E$32,"Ambos")+COUNTIFS('S2'!$B$6:$B$23,$A59,'S2'!$E$6:$E$23,"Diego")+COUNTIFS('S2'!$B$6:$B$23,$A59,'S2'!$E$6:$E$23,"Ambos")+COUNTIFS('S3'!$B$6:$B$24,$A59,'S3'!$E$6:$E$24,"Diego")+COUNTIFS('S3'!$B$6:$B$24,$A59,'S3'!$E$6:$E$24,"Ambos")+COUNTIFS('S4'!$B$6:$B$22,$A59,'S4'!$E$6:$E$22,"Diego")+COUNTIFS('S4'!$B$6:$B$22,$A59,'S4'!$E$6:$E$22,"Ambos")+COUNTIFS('S5'!$B$6:$B$20,$A59,'S5'!$E$6:$E$20,"Diego")+COUNTIFS('S5'!$B$6:$B$20,$A59,'S5'!$E$6:$E$20,"Ambos")+COUNTIFS('S6'!$B$6:$B$17,$A59,'S6'!$E$6:$E$17,"Diego")+COUNTIFS('S6'!$B$6:$B$17,$A59,'S6'!$E$6:$E$17,"Ambos")+COUNTIFS('S7'!$B$6:$B$19,$A59,'S7'!$E$6:$E$19,"Diego")+COUNTIFS('S7'!$B$6:$B$19,$A59,'S7'!$E$6:$E$19,"Ambos")+COUNTIFS('S8'!$B$6:$B$23,$A59,'S8'!$E$6:$E$23,"Diego")+COUNTIFS('S8'!$B$6:$B$23,$A59,'S8'!$E$6:$E$23,"Ambos")+COUNTIFS('S9'!$B$6:$B$15,$A59,'S9'!$E$6:$E$15,"Diego")+COUNTIFS('S9'!$B$6:$B$15,$A59,'S9'!$E$6:$E$15,"Ambos")+COUNTIFS('S10'!$B$6:$B$13,$A59,'S10'!$E$6:$E$13,"Diego")+COUNTIFS('S10'!$B$6:$B$13,$A59,'S10'!$E$6:$E$13,"Ambos")+COUNTIFS('Holgura'!$B$6:$B$11,$A59,'Holgura'!$E$6:$E$11,"Diego")+COUNTIFS('Holgura'!$B$6:$B$11,$A59,'Holgura'!$E$6:$E$11,"Ambos")+COUNTIFS('Entrega'!$B$6:$B$9,$A59,'Entrega'!$E$6:$E$9,"Diego")+COUNTIFS('Entrega'!$B$6:$B$9,$A59,'Entrega'!$E$6:$E$9,"Ambos")+COUNTIFS('Defensa'!$B$6:$B$10,$A59,'Defensa'!$E$6:$E$10,"Diego")+COUNTIFS('Defensa'!$B$6:$B$10,$A59,'Defensa'!$E$6:$E$10,"Ambos")</f>
         <v/>
       </c>
     </row>
@@ -10275,19 +10296,19 @@
         <v/>
       </c>
       <c r="D60" s="21">
-        <f>SUMIFS('S1'!$I$6:$I$32,'S1'!$B$6:$B$32,$A60,'S1'!$E$6:$E$32,"Víctor")+SUMIFS('S1'!$I$6:$I$32,'S1'!$B$6:$B$32,$A60,'S1'!$E$6:$E$32,"Ambos")+SUMIFS('S2'!$I$6:$I$23,'S2'!$B$6:$B$23,$A60,'S2'!$E$6:$E$23,"Víctor")+SUMIFS('S2'!$I$6:$I$23,'S2'!$B$6:$B$23,$A60,'S2'!$E$6:$E$23,"Ambos")+SUMIFS('S3'!$I$6:$I$19,'S3'!$B$6:$B$19,$A60,'S3'!$E$6:$E$19,"Víctor")+SUMIFS('S3'!$I$6:$I$19,'S3'!$B$6:$B$19,$A60,'S3'!$E$6:$E$19,"Ambos")+SUMIFS('S4'!$I$6:$I$20,'S4'!$B$6:$B$20,$A60,'S4'!$E$6:$E$20,"Víctor")+SUMIFS('S4'!$I$6:$I$20,'S4'!$B$6:$B$20,$A60,'S4'!$E$6:$E$20,"Ambos")+SUMIFS('S5'!$I$6:$I$20,'S5'!$B$6:$B$20,$A60,'S5'!$E$6:$E$20,"Víctor")+SUMIFS('S5'!$I$6:$I$20,'S5'!$B$6:$B$20,$A60,'S5'!$E$6:$E$20,"Ambos")+SUMIFS('S6'!$I$6:$I$17,'S6'!$B$6:$B$17,$A60,'S6'!$E$6:$E$17,"Víctor")+SUMIFS('S6'!$I$6:$I$17,'S6'!$B$6:$B$17,$A60,'S6'!$E$6:$E$17,"Ambos")+SUMIFS('S7'!$I$6:$I$19,'S7'!$B$6:$B$19,$A60,'S7'!$E$6:$E$19,"Víctor")+SUMIFS('S7'!$I$6:$I$19,'S7'!$B$6:$B$19,$A60,'S7'!$E$6:$E$19,"Ambos")+SUMIFS('S8'!$I$6:$I$23,'S8'!$B$6:$B$23,$A60,'S8'!$E$6:$E$23,"Víctor")+SUMIFS('S8'!$I$6:$I$23,'S8'!$B$6:$B$23,$A60,'S8'!$E$6:$E$23,"Ambos")+SUMIFS('S9'!$I$6:$I$15,'S9'!$B$6:$B$15,$A60,'S9'!$E$6:$E$15,"Víctor")+SUMIFS('S9'!$I$6:$I$15,'S9'!$B$6:$B$15,$A60,'S9'!$E$6:$E$15,"Ambos")+SUMIFS('S10'!$I$6:$I$13,'S10'!$B$6:$B$13,$A60,'S10'!$E$6:$E$13,"Víctor")+SUMIFS('S10'!$I$6:$I$13,'S10'!$B$6:$B$13,$A60,'S10'!$E$6:$E$13,"Ambos")+SUMIFS('Holgura'!$I$6:$I$11,'Holgura'!$B$6:$B$11,$A60,'Holgura'!$E$6:$E$11,"Víctor")+SUMIFS('Holgura'!$I$6:$I$11,'Holgura'!$B$6:$B$11,$A60,'Holgura'!$E$6:$E$11,"Ambos")+SUMIFS('Entrega'!$I$6:$I$9,'Entrega'!$B$6:$B$9,$A60,'Entrega'!$E$6:$E$9,"Víctor")+SUMIFS('Entrega'!$I$6:$I$9,'Entrega'!$B$6:$B$9,$A60,'Entrega'!$E$6:$E$9,"Ambos")+SUMIFS('Defensa'!$I$6:$I$10,'Defensa'!$B$6:$B$10,$A60,'Defensa'!$E$6:$E$10,"Víctor")+SUMIFS('Defensa'!$I$6:$I$10,'Defensa'!$B$6:$B$10,$A60,'Defensa'!$E$6:$E$10,"Ambos")</f>
+        <f>SUMIFS('S1'!$I$6:$I$32,'S1'!$B$6:$B$32,$A60,'S1'!$E$6:$E$32,"Víctor")+SUMIFS('S1'!$I$6:$I$32,'S1'!$B$6:$B$32,$A60,'S1'!$E$6:$E$32,"Ambos")+SUMIFS('S2'!$I$6:$I$23,'S2'!$B$6:$B$23,$A60,'S2'!$E$6:$E$23,"Víctor")+SUMIFS('S2'!$I$6:$I$23,'S2'!$B$6:$B$23,$A60,'S2'!$E$6:$E$23,"Ambos")+SUMIFS('S3'!$I$6:$I$24,'S3'!$B$6:$B$24,$A60,'S3'!$E$6:$E$24,"Víctor")+SUMIFS('S3'!$I$6:$I$24,'S3'!$B$6:$B$24,$A60,'S3'!$E$6:$E$24,"Ambos")+SUMIFS('S4'!$I$6:$I$22,'S4'!$B$6:$B$22,$A60,'S4'!$E$6:$E$22,"Víctor")+SUMIFS('S4'!$I$6:$I$22,'S4'!$B$6:$B$22,$A60,'S4'!$E$6:$E$22,"Ambos")+SUMIFS('S5'!$I$6:$I$20,'S5'!$B$6:$B$20,$A60,'S5'!$E$6:$E$20,"Víctor")+SUMIFS('S5'!$I$6:$I$20,'S5'!$B$6:$B$20,$A60,'S5'!$E$6:$E$20,"Ambos")+SUMIFS('S6'!$I$6:$I$17,'S6'!$B$6:$B$17,$A60,'S6'!$E$6:$E$17,"Víctor")+SUMIFS('S6'!$I$6:$I$17,'S6'!$B$6:$B$17,$A60,'S6'!$E$6:$E$17,"Ambos")+SUMIFS('S7'!$I$6:$I$19,'S7'!$B$6:$B$19,$A60,'S7'!$E$6:$E$19,"Víctor")+SUMIFS('S7'!$I$6:$I$19,'S7'!$B$6:$B$19,$A60,'S7'!$E$6:$E$19,"Ambos")+SUMIFS('S8'!$I$6:$I$23,'S8'!$B$6:$B$23,$A60,'S8'!$E$6:$E$23,"Víctor")+SUMIFS('S8'!$I$6:$I$23,'S8'!$B$6:$B$23,$A60,'S8'!$E$6:$E$23,"Ambos")+SUMIFS('S9'!$I$6:$I$15,'S9'!$B$6:$B$15,$A60,'S9'!$E$6:$E$15,"Víctor")+SUMIFS('S9'!$I$6:$I$15,'S9'!$B$6:$B$15,$A60,'S9'!$E$6:$E$15,"Ambos")+SUMIFS('S10'!$I$6:$I$13,'S10'!$B$6:$B$13,$A60,'S10'!$E$6:$E$13,"Víctor")+SUMIFS('S10'!$I$6:$I$13,'S10'!$B$6:$B$13,$A60,'S10'!$E$6:$E$13,"Ambos")+SUMIFS('Holgura'!$I$6:$I$11,'Holgura'!$B$6:$B$11,$A60,'Holgura'!$E$6:$E$11,"Víctor")+SUMIFS('Holgura'!$I$6:$I$11,'Holgura'!$B$6:$B$11,$A60,'Holgura'!$E$6:$E$11,"Ambos")+SUMIFS('Entrega'!$I$6:$I$9,'Entrega'!$B$6:$B$9,$A60,'Entrega'!$E$6:$E$9,"Víctor")+SUMIFS('Entrega'!$I$6:$I$9,'Entrega'!$B$6:$B$9,$A60,'Entrega'!$E$6:$E$9,"Ambos")+SUMIFS('Defensa'!$I$6:$I$10,'Defensa'!$B$6:$B$10,$A60,'Defensa'!$E$6:$E$10,"Víctor")+SUMIFS('Defensa'!$I$6:$I$10,'Defensa'!$B$6:$B$10,$A60,'Defensa'!$E$6:$E$10,"Ambos")</f>
         <v/>
       </c>
       <c r="E60" s="21">
-        <f>SUMIFS('S1'!$I$6:$I$32,'S1'!$B$6:$B$32,$A60,'S1'!$E$6:$E$32,"Diego")+SUMIFS('S1'!$I$6:$I$32,'S1'!$B$6:$B$32,$A60,'S1'!$E$6:$E$32,"Ambos")+SUMIFS('S2'!$I$6:$I$23,'S2'!$B$6:$B$23,$A60,'S2'!$E$6:$E$23,"Diego")+SUMIFS('S2'!$I$6:$I$23,'S2'!$B$6:$B$23,$A60,'S2'!$E$6:$E$23,"Ambos")+SUMIFS('S3'!$I$6:$I$19,'S3'!$B$6:$B$19,$A60,'S3'!$E$6:$E$19,"Diego")+SUMIFS('S3'!$I$6:$I$19,'S3'!$B$6:$B$19,$A60,'S3'!$E$6:$E$19,"Ambos")+SUMIFS('S4'!$I$6:$I$20,'S4'!$B$6:$B$20,$A60,'S4'!$E$6:$E$20,"Diego")+SUMIFS('S4'!$I$6:$I$20,'S4'!$B$6:$B$20,$A60,'S4'!$E$6:$E$20,"Ambos")+SUMIFS('S5'!$I$6:$I$20,'S5'!$B$6:$B$20,$A60,'S5'!$E$6:$E$20,"Diego")+SUMIFS('S5'!$I$6:$I$20,'S5'!$B$6:$B$20,$A60,'S5'!$E$6:$E$20,"Ambos")+SUMIFS('S6'!$I$6:$I$17,'S6'!$B$6:$B$17,$A60,'S6'!$E$6:$E$17,"Diego")+SUMIFS('S6'!$I$6:$I$17,'S6'!$B$6:$B$17,$A60,'S6'!$E$6:$E$17,"Ambos")+SUMIFS('S7'!$I$6:$I$19,'S7'!$B$6:$B$19,$A60,'S7'!$E$6:$E$19,"Diego")+SUMIFS('S7'!$I$6:$I$19,'S7'!$B$6:$B$19,$A60,'S7'!$E$6:$E$19,"Ambos")+SUMIFS('S8'!$I$6:$I$23,'S8'!$B$6:$B$23,$A60,'S8'!$E$6:$E$23,"Diego")+SUMIFS('S8'!$I$6:$I$23,'S8'!$B$6:$B$23,$A60,'S8'!$E$6:$E$23,"Ambos")+SUMIFS('S9'!$I$6:$I$15,'S9'!$B$6:$B$15,$A60,'S9'!$E$6:$E$15,"Diego")+SUMIFS('S9'!$I$6:$I$15,'S9'!$B$6:$B$15,$A60,'S9'!$E$6:$E$15,"Ambos")+SUMIFS('S10'!$I$6:$I$13,'S10'!$B$6:$B$13,$A60,'S10'!$E$6:$E$13,"Diego")+SUMIFS('S10'!$I$6:$I$13,'S10'!$B$6:$B$13,$A60,'S10'!$E$6:$E$13,"Ambos")+SUMIFS('Holgura'!$I$6:$I$11,'Holgura'!$B$6:$B$11,$A60,'Holgura'!$E$6:$E$11,"Diego")+SUMIFS('Holgura'!$I$6:$I$11,'Holgura'!$B$6:$B$11,$A60,'Holgura'!$E$6:$E$11,"Ambos")+SUMIFS('Entrega'!$I$6:$I$9,'Entrega'!$B$6:$B$9,$A60,'Entrega'!$E$6:$E$9,"Diego")+SUMIFS('Entrega'!$I$6:$I$9,'Entrega'!$B$6:$B$9,$A60,'Entrega'!$E$6:$E$9,"Ambos")+SUMIFS('Defensa'!$I$6:$I$10,'Defensa'!$B$6:$B$10,$A60,'Defensa'!$E$6:$E$10,"Diego")+SUMIFS('Defensa'!$I$6:$I$10,'Defensa'!$B$6:$B$10,$A60,'Defensa'!$E$6:$E$10,"Ambos")</f>
+        <f>SUMIFS('S1'!$I$6:$I$32,'S1'!$B$6:$B$32,$A60,'S1'!$E$6:$E$32,"Diego")+SUMIFS('S1'!$I$6:$I$32,'S1'!$B$6:$B$32,$A60,'S1'!$E$6:$E$32,"Ambos")+SUMIFS('S2'!$I$6:$I$23,'S2'!$B$6:$B$23,$A60,'S2'!$E$6:$E$23,"Diego")+SUMIFS('S2'!$I$6:$I$23,'S2'!$B$6:$B$23,$A60,'S2'!$E$6:$E$23,"Ambos")+SUMIFS('S3'!$I$6:$I$24,'S3'!$B$6:$B$24,$A60,'S3'!$E$6:$E$24,"Diego")+SUMIFS('S3'!$I$6:$I$24,'S3'!$B$6:$B$24,$A60,'S3'!$E$6:$E$24,"Ambos")+SUMIFS('S4'!$I$6:$I$22,'S4'!$B$6:$B$22,$A60,'S4'!$E$6:$E$22,"Diego")+SUMIFS('S4'!$I$6:$I$22,'S4'!$B$6:$B$22,$A60,'S4'!$E$6:$E$22,"Ambos")+SUMIFS('S5'!$I$6:$I$20,'S5'!$B$6:$B$20,$A60,'S5'!$E$6:$E$20,"Diego")+SUMIFS('S5'!$I$6:$I$20,'S5'!$B$6:$B$20,$A60,'S5'!$E$6:$E$20,"Ambos")+SUMIFS('S6'!$I$6:$I$17,'S6'!$B$6:$B$17,$A60,'S6'!$E$6:$E$17,"Diego")+SUMIFS('S6'!$I$6:$I$17,'S6'!$B$6:$B$17,$A60,'S6'!$E$6:$E$17,"Ambos")+SUMIFS('S7'!$I$6:$I$19,'S7'!$B$6:$B$19,$A60,'S7'!$E$6:$E$19,"Diego")+SUMIFS('S7'!$I$6:$I$19,'S7'!$B$6:$B$19,$A60,'S7'!$E$6:$E$19,"Ambos")+SUMIFS('S8'!$I$6:$I$23,'S8'!$B$6:$B$23,$A60,'S8'!$E$6:$E$23,"Diego")+SUMIFS('S8'!$I$6:$I$23,'S8'!$B$6:$B$23,$A60,'S8'!$E$6:$E$23,"Ambos")+SUMIFS('S9'!$I$6:$I$15,'S9'!$B$6:$B$15,$A60,'S9'!$E$6:$E$15,"Diego")+SUMIFS('S9'!$I$6:$I$15,'S9'!$B$6:$B$15,$A60,'S9'!$E$6:$E$15,"Ambos")+SUMIFS('S10'!$I$6:$I$13,'S10'!$B$6:$B$13,$A60,'S10'!$E$6:$E$13,"Diego")+SUMIFS('S10'!$I$6:$I$13,'S10'!$B$6:$B$13,$A60,'S10'!$E$6:$E$13,"Ambos")+SUMIFS('Holgura'!$I$6:$I$11,'Holgura'!$B$6:$B$11,$A60,'Holgura'!$E$6:$E$11,"Diego")+SUMIFS('Holgura'!$I$6:$I$11,'Holgura'!$B$6:$B$11,$A60,'Holgura'!$E$6:$E$11,"Ambos")+SUMIFS('Entrega'!$I$6:$I$9,'Entrega'!$B$6:$B$9,$A60,'Entrega'!$E$6:$E$9,"Diego")+SUMIFS('Entrega'!$I$6:$I$9,'Entrega'!$B$6:$B$9,$A60,'Entrega'!$E$6:$E$9,"Ambos")+SUMIFS('Defensa'!$I$6:$I$10,'Defensa'!$B$6:$B$10,$A60,'Defensa'!$E$6:$E$10,"Diego")+SUMIFS('Defensa'!$I$6:$I$10,'Defensa'!$B$6:$B$10,$A60,'Defensa'!$E$6:$E$10,"Ambos")</f>
         <v/>
       </c>
       <c r="F60" s="21">
-        <f>COUNTIFS('S1'!$B$6:$B$32,$A60,'S1'!$E$6:$E$32,"Víctor")+COUNTIFS('S1'!$B$6:$B$32,$A60,'S1'!$E$6:$E$32,"Ambos")+COUNTIFS('S2'!$B$6:$B$23,$A60,'S2'!$E$6:$E$23,"Víctor")+COUNTIFS('S2'!$B$6:$B$23,$A60,'S2'!$E$6:$E$23,"Ambos")+COUNTIFS('S3'!$B$6:$B$19,$A60,'S3'!$E$6:$E$19,"Víctor")+COUNTIFS('S3'!$B$6:$B$19,$A60,'S3'!$E$6:$E$19,"Ambos")+COUNTIFS('S4'!$B$6:$B$20,$A60,'S4'!$E$6:$E$20,"Víctor")+COUNTIFS('S4'!$B$6:$B$20,$A60,'S4'!$E$6:$E$20,"Ambos")+COUNTIFS('S5'!$B$6:$B$20,$A60,'S5'!$E$6:$E$20,"Víctor")+COUNTIFS('S5'!$B$6:$B$20,$A60,'S5'!$E$6:$E$20,"Ambos")+COUNTIFS('S6'!$B$6:$B$17,$A60,'S6'!$E$6:$E$17,"Víctor")+COUNTIFS('S6'!$B$6:$B$17,$A60,'S6'!$E$6:$E$17,"Ambos")+COUNTIFS('S7'!$B$6:$B$19,$A60,'S7'!$E$6:$E$19,"Víctor")+COUNTIFS('S7'!$B$6:$B$19,$A60,'S7'!$E$6:$E$19,"Ambos")+COUNTIFS('S8'!$B$6:$B$23,$A60,'S8'!$E$6:$E$23,"Víctor")+COUNTIFS('S8'!$B$6:$B$23,$A60,'S8'!$E$6:$E$23,"Ambos")+COUNTIFS('S9'!$B$6:$B$15,$A60,'S9'!$E$6:$E$15,"Víctor")+COUNTIFS('S9'!$B$6:$B$15,$A60,'S9'!$E$6:$E$15,"Ambos")+COUNTIFS('S10'!$B$6:$B$13,$A60,'S10'!$E$6:$E$13,"Víctor")+COUNTIFS('S10'!$B$6:$B$13,$A60,'S10'!$E$6:$E$13,"Ambos")+COUNTIFS('Holgura'!$B$6:$B$11,$A60,'Holgura'!$E$6:$E$11,"Víctor")+COUNTIFS('Holgura'!$B$6:$B$11,$A60,'Holgura'!$E$6:$E$11,"Ambos")+COUNTIFS('Entrega'!$B$6:$B$9,$A60,'Entrega'!$E$6:$E$9,"Víctor")+COUNTIFS('Entrega'!$B$6:$B$9,$A60,'Entrega'!$E$6:$E$9,"Ambos")+COUNTIFS('Defensa'!$B$6:$B$10,$A60,'Defensa'!$E$6:$E$10,"Víctor")+COUNTIFS('Defensa'!$B$6:$B$10,$A60,'Defensa'!$E$6:$E$10,"Ambos")</f>
+        <f>COUNTIFS('S1'!$B$6:$B$32,$A60,'S1'!$E$6:$E$32,"Víctor")+COUNTIFS('S1'!$B$6:$B$32,$A60,'S1'!$E$6:$E$32,"Ambos")+COUNTIFS('S2'!$B$6:$B$23,$A60,'S2'!$E$6:$E$23,"Víctor")+COUNTIFS('S2'!$B$6:$B$23,$A60,'S2'!$E$6:$E$23,"Ambos")+COUNTIFS('S3'!$B$6:$B$24,$A60,'S3'!$E$6:$E$24,"Víctor")+COUNTIFS('S3'!$B$6:$B$24,$A60,'S3'!$E$6:$E$24,"Ambos")+COUNTIFS('S4'!$B$6:$B$22,$A60,'S4'!$E$6:$E$22,"Víctor")+COUNTIFS('S4'!$B$6:$B$22,$A60,'S4'!$E$6:$E$22,"Ambos")+COUNTIFS('S5'!$B$6:$B$20,$A60,'S5'!$E$6:$E$20,"Víctor")+COUNTIFS('S5'!$B$6:$B$20,$A60,'S5'!$E$6:$E$20,"Ambos")+COUNTIFS('S6'!$B$6:$B$17,$A60,'S6'!$E$6:$E$17,"Víctor")+COUNTIFS('S6'!$B$6:$B$17,$A60,'S6'!$E$6:$E$17,"Ambos")+COUNTIFS('S7'!$B$6:$B$19,$A60,'S7'!$E$6:$E$19,"Víctor")+COUNTIFS('S7'!$B$6:$B$19,$A60,'S7'!$E$6:$E$19,"Ambos")+COUNTIFS('S8'!$B$6:$B$23,$A60,'S8'!$E$6:$E$23,"Víctor")+COUNTIFS('S8'!$B$6:$B$23,$A60,'S8'!$E$6:$E$23,"Ambos")+COUNTIFS('S9'!$B$6:$B$15,$A60,'S9'!$E$6:$E$15,"Víctor")+COUNTIFS('S9'!$B$6:$B$15,$A60,'S9'!$E$6:$E$15,"Ambos")+COUNTIFS('S10'!$B$6:$B$13,$A60,'S10'!$E$6:$E$13,"Víctor")+COUNTIFS('S10'!$B$6:$B$13,$A60,'S10'!$E$6:$E$13,"Ambos")+COUNTIFS('Holgura'!$B$6:$B$11,$A60,'Holgura'!$E$6:$E$11,"Víctor")+COUNTIFS('Holgura'!$B$6:$B$11,$A60,'Holgura'!$E$6:$E$11,"Ambos")+COUNTIFS('Entrega'!$B$6:$B$9,$A60,'Entrega'!$E$6:$E$9,"Víctor")+COUNTIFS('Entrega'!$B$6:$B$9,$A60,'Entrega'!$E$6:$E$9,"Ambos")+COUNTIFS('Defensa'!$B$6:$B$10,$A60,'Defensa'!$E$6:$E$10,"Víctor")+COUNTIFS('Defensa'!$B$6:$B$10,$A60,'Defensa'!$E$6:$E$10,"Ambos")</f>
         <v/>
       </c>
       <c r="G60" s="21">
-        <f>COUNTIFS('S1'!$B$6:$B$32,$A60,'S1'!$E$6:$E$32,"Diego")+COUNTIFS('S1'!$B$6:$B$32,$A60,'S1'!$E$6:$E$32,"Ambos")+COUNTIFS('S2'!$B$6:$B$23,$A60,'S2'!$E$6:$E$23,"Diego")+COUNTIFS('S2'!$B$6:$B$23,$A60,'S2'!$E$6:$E$23,"Ambos")+COUNTIFS('S3'!$B$6:$B$19,$A60,'S3'!$E$6:$E$19,"Diego")+COUNTIFS('S3'!$B$6:$B$19,$A60,'S3'!$E$6:$E$19,"Ambos")+COUNTIFS('S4'!$B$6:$B$20,$A60,'S4'!$E$6:$E$20,"Diego")+COUNTIFS('S4'!$B$6:$B$20,$A60,'S4'!$E$6:$E$20,"Ambos")+COUNTIFS('S5'!$B$6:$B$20,$A60,'S5'!$E$6:$E$20,"Diego")+COUNTIFS('S5'!$B$6:$B$20,$A60,'S5'!$E$6:$E$20,"Ambos")+COUNTIFS('S6'!$B$6:$B$17,$A60,'S6'!$E$6:$E$17,"Diego")+COUNTIFS('S6'!$B$6:$B$17,$A60,'S6'!$E$6:$E$17,"Ambos")+COUNTIFS('S7'!$B$6:$B$19,$A60,'S7'!$E$6:$E$19,"Diego")+COUNTIFS('S7'!$B$6:$B$19,$A60,'S7'!$E$6:$E$19,"Ambos")+COUNTIFS('S8'!$B$6:$B$23,$A60,'S8'!$E$6:$E$23,"Diego")+COUNTIFS('S8'!$B$6:$B$23,$A60,'S8'!$E$6:$E$23,"Ambos")+COUNTIFS('S9'!$B$6:$B$15,$A60,'S9'!$E$6:$E$15,"Diego")+COUNTIFS('S9'!$B$6:$B$15,$A60,'S9'!$E$6:$E$15,"Ambos")+COUNTIFS('S10'!$B$6:$B$13,$A60,'S10'!$E$6:$E$13,"Diego")+COUNTIFS('S10'!$B$6:$B$13,$A60,'S10'!$E$6:$E$13,"Ambos")+COUNTIFS('Holgura'!$B$6:$B$11,$A60,'Holgura'!$E$6:$E$11,"Diego")+COUNTIFS('Holgura'!$B$6:$B$11,$A60,'Holgura'!$E$6:$E$11,"Ambos")+COUNTIFS('Entrega'!$B$6:$B$9,$A60,'Entrega'!$E$6:$E$9,"Diego")+COUNTIFS('Entrega'!$B$6:$B$9,$A60,'Entrega'!$E$6:$E$9,"Ambos")+COUNTIFS('Defensa'!$B$6:$B$10,$A60,'Defensa'!$E$6:$E$10,"Diego")+COUNTIFS('Defensa'!$B$6:$B$10,$A60,'Defensa'!$E$6:$E$10,"Ambos")</f>
+        <f>COUNTIFS('S1'!$B$6:$B$32,$A60,'S1'!$E$6:$E$32,"Diego")+COUNTIFS('S1'!$B$6:$B$32,$A60,'S1'!$E$6:$E$32,"Ambos")+COUNTIFS('S2'!$B$6:$B$23,$A60,'S2'!$E$6:$E$23,"Diego")+COUNTIFS('S2'!$B$6:$B$23,$A60,'S2'!$E$6:$E$23,"Ambos")+COUNTIFS('S3'!$B$6:$B$24,$A60,'S3'!$E$6:$E$24,"Diego")+COUNTIFS('S3'!$B$6:$B$24,$A60,'S3'!$E$6:$E$24,"Ambos")+COUNTIFS('S4'!$B$6:$B$22,$A60,'S4'!$E$6:$E$22,"Diego")+COUNTIFS('S4'!$B$6:$B$22,$A60,'S4'!$E$6:$E$22,"Ambos")+COUNTIFS('S5'!$B$6:$B$20,$A60,'S5'!$E$6:$E$20,"Diego")+COUNTIFS('S5'!$B$6:$B$20,$A60,'S5'!$E$6:$E$20,"Ambos")+COUNTIFS('S6'!$B$6:$B$17,$A60,'S6'!$E$6:$E$17,"Diego")+COUNTIFS('S6'!$B$6:$B$17,$A60,'S6'!$E$6:$E$17,"Ambos")+COUNTIFS('S7'!$B$6:$B$19,$A60,'S7'!$E$6:$E$19,"Diego")+COUNTIFS('S7'!$B$6:$B$19,$A60,'S7'!$E$6:$E$19,"Ambos")+COUNTIFS('S8'!$B$6:$B$23,$A60,'S8'!$E$6:$E$23,"Diego")+COUNTIFS('S8'!$B$6:$B$23,$A60,'S8'!$E$6:$E$23,"Ambos")+COUNTIFS('S9'!$B$6:$B$15,$A60,'S9'!$E$6:$E$15,"Diego")+COUNTIFS('S9'!$B$6:$B$15,$A60,'S9'!$E$6:$E$15,"Ambos")+COUNTIFS('S10'!$B$6:$B$13,$A60,'S10'!$E$6:$E$13,"Diego")+COUNTIFS('S10'!$B$6:$B$13,$A60,'S10'!$E$6:$E$13,"Ambos")+COUNTIFS('Holgura'!$B$6:$B$11,$A60,'Holgura'!$E$6:$E$11,"Diego")+COUNTIFS('Holgura'!$B$6:$B$11,$A60,'Holgura'!$E$6:$E$11,"Ambos")+COUNTIFS('Entrega'!$B$6:$B$9,$A60,'Entrega'!$E$6:$E$9,"Diego")+COUNTIFS('Entrega'!$B$6:$B$9,$A60,'Entrega'!$E$6:$E$9,"Ambos")+COUNTIFS('Defensa'!$B$6:$B$10,$A60,'Defensa'!$E$6:$E$10,"Diego")+COUNTIFS('Defensa'!$B$6:$B$10,$A60,'Defensa'!$E$6:$E$10,"Ambos")</f>
         <v/>
       </c>
     </row>
@@ -10304,19 +10325,19 @@
         <v/>
       </c>
       <c r="D61" s="21">
-        <f>SUMIFS('S1'!$I$6:$I$32,'S1'!$B$6:$B$32,$A61,'S1'!$E$6:$E$32,"Víctor")+SUMIFS('S1'!$I$6:$I$32,'S1'!$B$6:$B$32,$A61,'S1'!$E$6:$E$32,"Ambos")+SUMIFS('S2'!$I$6:$I$23,'S2'!$B$6:$B$23,$A61,'S2'!$E$6:$E$23,"Víctor")+SUMIFS('S2'!$I$6:$I$23,'S2'!$B$6:$B$23,$A61,'S2'!$E$6:$E$23,"Ambos")+SUMIFS('S3'!$I$6:$I$19,'S3'!$B$6:$B$19,$A61,'S3'!$E$6:$E$19,"Víctor")+SUMIFS('S3'!$I$6:$I$19,'S3'!$B$6:$B$19,$A61,'S3'!$E$6:$E$19,"Ambos")+SUMIFS('S4'!$I$6:$I$20,'S4'!$B$6:$B$20,$A61,'S4'!$E$6:$E$20,"Víctor")+SUMIFS('S4'!$I$6:$I$20,'S4'!$B$6:$B$20,$A61,'S4'!$E$6:$E$20,"Ambos")+SUMIFS('S5'!$I$6:$I$20,'S5'!$B$6:$B$20,$A61,'S5'!$E$6:$E$20,"Víctor")+SUMIFS('S5'!$I$6:$I$20,'S5'!$B$6:$B$20,$A61,'S5'!$E$6:$E$20,"Ambos")+SUMIFS('S6'!$I$6:$I$17,'S6'!$B$6:$B$17,$A61,'S6'!$E$6:$E$17,"Víctor")+SUMIFS('S6'!$I$6:$I$17,'S6'!$B$6:$B$17,$A61,'S6'!$E$6:$E$17,"Ambos")+SUMIFS('S7'!$I$6:$I$19,'S7'!$B$6:$B$19,$A61,'S7'!$E$6:$E$19,"Víctor")+SUMIFS('S7'!$I$6:$I$19,'S7'!$B$6:$B$19,$A61,'S7'!$E$6:$E$19,"Ambos")+SUMIFS('S8'!$I$6:$I$23,'S8'!$B$6:$B$23,$A61,'S8'!$E$6:$E$23,"Víctor")+SUMIFS('S8'!$I$6:$I$23,'S8'!$B$6:$B$23,$A61,'S8'!$E$6:$E$23,"Ambos")+SUMIFS('S9'!$I$6:$I$15,'S9'!$B$6:$B$15,$A61,'S9'!$E$6:$E$15,"Víctor")+SUMIFS('S9'!$I$6:$I$15,'S9'!$B$6:$B$15,$A61,'S9'!$E$6:$E$15,"Ambos")+SUMIFS('S10'!$I$6:$I$13,'S10'!$B$6:$B$13,$A61,'S10'!$E$6:$E$13,"Víctor")+SUMIFS('S10'!$I$6:$I$13,'S10'!$B$6:$B$13,$A61,'S10'!$E$6:$E$13,"Ambos")+SUMIFS('Holgura'!$I$6:$I$11,'Holgura'!$B$6:$B$11,$A61,'Holgura'!$E$6:$E$11,"Víctor")+SUMIFS('Holgura'!$I$6:$I$11,'Holgura'!$B$6:$B$11,$A61,'Holgura'!$E$6:$E$11,"Ambos")+SUMIFS('Entrega'!$I$6:$I$9,'Entrega'!$B$6:$B$9,$A61,'Entrega'!$E$6:$E$9,"Víctor")+SUMIFS('Entrega'!$I$6:$I$9,'Entrega'!$B$6:$B$9,$A61,'Entrega'!$E$6:$E$9,"Ambos")+SUMIFS('Defensa'!$I$6:$I$10,'Defensa'!$B$6:$B$10,$A61,'Defensa'!$E$6:$E$10,"Víctor")+SUMIFS('Defensa'!$I$6:$I$10,'Defensa'!$B$6:$B$10,$A61,'Defensa'!$E$6:$E$10,"Ambos")</f>
+        <f>SUMIFS('S1'!$I$6:$I$32,'S1'!$B$6:$B$32,$A61,'S1'!$E$6:$E$32,"Víctor")+SUMIFS('S1'!$I$6:$I$32,'S1'!$B$6:$B$32,$A61,'S1'!$E$6:$E$32,"Ambos")+SUMIFS('S2'!$I$6:$I$23,'S2'!$B$6:$B$23,$A61,'S2'!$E$6:$E$23,"Víctor")+SUMIFS('S2'!$I$6:$I$23,'S2'!$B$6:$B$23,$A61,'S2'!$E$6:$E$23,"Ambos")+SUMIFS('S3'!$I$6:$I$24,'S3'!$B$6:$B$24,$A61,'S3'!$E$6:$E$24,"Víctor")+SUMIFS('S3'!$I$6:$I$24,'S3'!$B$6:$B$24,$A61,'S3'!$E$6:$E$24,"Ambos")+SUMIFS('S4'!$I$6:$I$22,'S4'!$B$6:$B$22,$A61,'S4'!$E$6:$E$22,"Víctor")+SUMIFS('S4'!$I$6:$I$22,'S4'!$B$6:$B$22,$A61,'S4'!$E$6:$E$22,"Ambos")+SUMIFS('S5'!$I$6:$I$20,'S5'!$B$6:$B$20,$A61,'S5'!$E$6:$E$20,"Víctor")+SUMIFS('S5'!$I$6:$I$20,'S5'!$B$6:$B$20,$A61,'S5'!$E$6:$E$20,"Ambos")+SUMIFS('S6'!$I$6:$I$17,'S6'!$B$6:$B$17,$A61,'S6'!$E$6:$E$17,"Víctor")+SUMIFS('S6'!$I$6:$I$17,'S6'!$B$6:$B$17,$A61,'S6'!$E$6:$E$17,"Ambos")+SUMIFS('S7'!$I$6:$I$19,'S7'!$B$6:$B$19,$A61,'S7'!$E$6:$E$19,"Víctor")+SUMIFS('S7'!$I$6:$I$19,'S7'!$B$6:$B$19,$A61,'S7'!$E$6:$E$19,"Ambos")+SUMIFS('S8'!$I$6:$I$23,'S8'!$B$6:$B$23,$A61,'S8'!$E$6:$E$23,"Víctor")+SUMIFS('S8'!$I$6:$I$23,'S8'!$B$6:$B$23,$A61,'S8'!$E$6:$E$23,"Ambos")+SUMIFS('S9'!$I$6:$I$15,'S9'!$B$6:$B$15,$A61,'S9'!$E$6:$E$15,"Víctor")+SUMIFS('S9'!$I$6:$I$15,'S9'!$B$6:$B$15,$A61,'S9'!$E$6:$E$15,"Ambos")+SUMIFS('S10'!$I$6:$I$13,'S10'!$B$6:$B$13,$A61,'S10'!$E$6:$E$13,"Víctor")+SUMIFS('S10'!$I$6:$I$13,'S10'!$B$6:$B$13,$A61,'S10'!$E$6:$E$13,"Ambos")+SUMIFS('Holgura'!$I$6:$I$11,'Holgura'!$B$6:$B$11,$A61,'Holgura'!$E$6:$E$11,"Víctor")+SUMIFS('Holgura'!$I$6:$I$11,'Holgura'!$B$6:$B$11,$A61,'Holgura'!$E$6:$E$11,"Ambos")+SUMIFS('Entrega'!$I$6:$I$9,'Entrega'!$B$6:$B$9,$A61,'Entrega'!$E$6:$E$9,"Víctor")+SUMIFS('Entrega'!$I$6:$I$9,'Entrega'!$B$6:$B$9,$A61,'Entrega'!$E$6:$E$9,"Ambos")+SUMIFS('Defensa'!$I$6:$I$10,'Defensa'!$B$6:$B$10,$A61,'Defensa'!$E$6:$E$10,"Víctor")+SUMIFS('Defensa'!$I$6:$I$10,'Defensa'!$B$6:$B$10,$A61,'Defensa'!$E$6:$E$10,"Ambos")</f>
         <v/>
       </c>
       <c r="E61" s="21">
-        <f>SUMIFS('S1'!$I$6:$I$32,'S1'!$B$6:$B$32,$A61,'S1'!$E$6:$E$32,"Diego")+SUMIFS('S1'!$I$6:$I$32,'S1'!$B$6:$B$32,$A61,'S1'!$E$6:$E$32,"Ambos")+SUMIFS('S2'!$I$6:$I$23,'S2'!$B$6:$B$23,$A61,'S2'!$E$6:$E$23,"Diego")+SUMIFS('S2'!$I$6:$I$23,'S2'!$B$6:$B$23,$A61,'S2'!$E$6:$E$23,"Ambos")+SUMIFS('S3'!$I$6:$I$19,'S3'!$B$6:$B$19,$A61,'S3'!$E$6:$E$19,"Diego")+SUMIFS('S3'!$I$6:$I$19,'S3'!$B$6:$B$19,$A61,'S3'!$E$6:$E$19,"Ambos")+SUMIFS('S4'!$I$6:$I$20,'S4'!$B$6:$B$20,$A61,'S4'!$E$6:$E$20,"Diego")+SUMIFS('S4'!$I$6:$I$20,'S4'!$B$6:$B$20,$A61,'S4'!$E$6:$E$20,"Ambos")+SUMIFS('S5'!$I$6:$I$20,'S5'!$B$6:$B$20,$A61,'S5'!$E$6:$E$20,"Diego")+SUMIFS('S5'!$I$6:$I$20,'S5'!$B$6:$B$20,$A61,'S5'!$E$6:$E$20,"Ambos")+SUMIFS('S6'!$I$6:$I$17,'S6'!$B$6:$B$17,$A61,'S6'!$E$6:$E$17,"Diego")+SUMIFS('S6'!$I$6:$I$17,'S6'!$B$6:$B$17,$A61,'S6'!$E$6:$E$17,"Ambos")+SUMIFS('S7'!$I$6:$I$19,'S7'!$B$6:$B$19,$A61,'S7'!$E$6:$E$19,"Diego")+SUMIFS('S7'!$I$6:$I$19,'S7'!$B$6:$B$19,$A61,'S7'!$E$6:$E$19,"Ambos")+SUMIFS('S8'!$I$6:$I$23,'S8'!$B$6:$B$23,$A61,'S8'!$E$6:$E$23,"Diego")+SUMIFS('S8'!$I$6:$I$23,'S8'!$B$6:$B$23,$A61,'S8'!$E$6:$E$23,"Ambos")+SUMIFS('S9'!$I$6:$I$15,'S9'!$B$6:$B$15,$A61,'S9'!$E$6:$E$15,"Diego")+SUMIFS('S9'!$I$6:$I$15,'S9'!$B$6:$B$15,$A61,'S9'!$E$6:$E$15,"Ambos")+SUMIFS('S10'!$I$6:$I$13,'S10'!$B$6:$B$13,$A61,'S10'!$E$6:$E$13,"Diego")+SUMIFS('S10'!$I$6:$I$13,'S10'!$B$6:$B$13,$A61,'S10'!$E$6:$E$13,"Ambos")+SUMIFS('Holgura'!$I$6:$I$11,'Holgura'!$B$6:$B$11,$A61,'Holgura'!$E$6:$E$11,"Diego")+SUMIFS('Holgura'!$I$6:$I$11,'Holgura'!$B$6:$B$11,$A61,'Holgura'!$E$6:$E$11,"Ambos")+SUMIFS('Entrega'!$I$6:$I$9,'Entrega'!$B$6:$B$9,$A61,'Entrega'!$E$6:$E$9,"Diego")+SUMIFS('Entrega'!$I$6:$I$9,'Entrega'!$B$6:$B$9,$A61,'Entrega'!$E$6:$E$9,"Ambos")+SUMIFS('Defensa'!$I$6:$I$10,'Defensa'!$B$6:$B$10,$A61,'Defensa'!$E$6:$E$10,"Diego")+SUMIFS('Defensa'!$I$6:$I$10,'Defensa'!$B$6:$B$10,$A61,'Defensa'!$E$6:$E$10,"Ambos")</f>
+        <f>SUMIFS('S1'!$I$6:$I$32,'S1'!$B$6:$B$32,$A61,'S1'!$E$6:$E$32,"Diego")+SUMIFS('S1'!$I$6:$I$32,'S1'!$B$6:$B$32,$A61,'S1'!$E$6:$E$32,"Ambos")+SUMIFS('S2'!$I$6:$I$23,'S2'!$B$6:$B$23,$A61,'S2'!$E$6:$E$23,"Diego")+SUMIFS('S2'!$I$6:$I$23,'S2'!$B$6:$B$23,$A61,'S2'!$E$6:$E$23,"Ambos")+SUMIFS('S3'!$I$6:$I$24,'S3'!$B$6:$B$24,$A61,'S3'!$E$6:$E$24,"Diego")+SUMIFS('S3'!$I$6:$I$24,'S3'!$B$6:$B$24,$A61,'S3'!$E$6:$E$24,"Ambos")+SUMIFS('S4'!$I$6:$I$22,'S4'!$B$6:$B$22,$A61,'S4'!$E$6:$E$22,"Diego")+SUMIFS('S4'!$I$6:$I$22,'S4'!$B$6:$B$22,$A61,'S4'!$E$6:$E$22,"Ambos")+SUMIFS('S5'!$I$6:$I$20,'S5'!$B$6:$B$20,$A61,'S5'!$E$6:$E$20,"Diego")+SUMIFS('S5'!$I$6:$I$20,'S5'!$B$6:$B$20,$A61,'S5'!$E$6:$E$20,"Ambos")+SUMIFS('S6'!$I$6:$I$17,'S6'!$B$6:$B$17,$A61,'S6'!$E$6:$E$17,"Diego")+SUMIFS('S6'!$I$6:$I$17,'S6'!$B$6:$B$17,$A61,'S6'!$E$6:$E$17,"Ambos")+SUMIFS('S7'!$I$6:$I$19,'S7'!$B$6:$B$19,$A61,'S7'!$E$6:$E$19,"Diego")+SUMIFS('S7'!$I$6:$I$19,'S7'!$B$6:$B$19,$A61,'S7'!$E$6:$E$19,"Ambos")+SUMIFS('S8'!$I$6:$I$23,'S8'!$B$6:$B$23,$A61,'S8'!$E$6:$E$23,"Diego")+SUMIFS('S8'!$I$6:$I$23,'S8'!$B$6:$B$23,$A61,'S8'!$E$6:$E$23,"Ambos")+SUMIFS('S9'!$I$6:$I$15,'S9'!$B$6:$B$15,$A61,'S9'!$E$6:$E$15,"Diego")+SUMIFS('S9'!$I$6:$I$15,'S9'!$B$6:$B$15,$A61,'S9'!$E$6:$E$15,"Ambos")+SUMIFS('S10'!$I$6:$I$13,'S10'!$B$6:$B$13,$A61,'S10'!$E$6:$E$13,"Diego")+SUMIFS('S10'!$I$6:$I$13,'S10'!$B$6:$B$13,$A61,'S10'!$E$6:$E$13,"Ambos")+SUMIFS('Holgura'!$I$6:$I$11,'Holgura'!$B$6:$B$11,$A61,'Holgura'!$E$6:$E$11,"Diego")+SUMIFS('Holgura'!$I$6:$I$11,'Holgura'!$B$6:$B$11,$A61,'Holgura'!$E$6:$E$11,"Ambos")+SUMIFS('Entrega'!$I$6:$I$9,'Entrega'!$B$6:$B$9,$A61,'Entrega'!$E$6:$E$9,"Diego")+SUMIFS('Entrega'!$I$6:$I$9,'Entrega'!$B$6:$B$9,$A61,'Entrega'!$E$6:$E$9,"Ambos")+SUMIFS('Defensa'!$I$6:$I$10,'Defensa'!$B$6:$B$10,$A61,'Defensa'!$E$6:$E$10,"Diego")+SUMIFS('Defensa'!$I$6:$I$10,'Defensa'!$B$6:$B$10,$A61,'Defensa'!$E$6:$E$10,"Ambos")</f>
         <v/>
       </c>
       <c r="F61" s="21">
-        <f>COUNTIFS('S1'!$B$6:$B$32,$A61,'S1'!$E$6:$E$32,"Víctor")+COUNTIFS('S1'!$B$6:$B$32,$A61,'S1'!$E$6:$E$32,"Ambos")+COUNTIFS('S2'!$B$6:$B$23,$A61,'S2'!$E$6:$E$23,"Víctor")+COUNTIFS('S2'!$B$6:$B$23,$A61,'S2'!$E$6:$E$23,"Ambos")+COUNTIFS('S3'!$B$6:$B$19,$A61,'S3'!$E$6:$E$19,"Víctor")+COUNTIFS('S3'!$B$6:$B$19,$A61,'S3'!$E$6:$E$19,"Ambos")+COUNTIFS('S4'!$B$6:$B$20,$A61,'S4'!$E$6:$E$20,"Víctor")+COUNTIFS('S4'!$B$6:$B$20,$A61,'S4'!$E$6:$E$20,"Ambos")+COUNTIFS('S5'!$B$6:$B$20,$A61,'S5'!$E$6:$E$20,"Víctor")+COUNTIFS('S5'!$B$6:$B$20,$A61,'S5'!$E$6:$E$20,"Ambos")+COUNTIFS('S6'!$B$6:$B$17,$A61,'S6'!$E$6:$E$17,"Víctor")+COUNTIFS('S6'!$B$6:$B$17,$A61,'S6'!$E$6:$E$17,"Ambos")+COUNTIFS('S7'!$B$6:$B$19,$A61,'S7'!$E$6:$E$19,"Víctor")+COUNTIFS('S7'!$B$6:$B$19,$A61,'S7'!$E$6:$E$19,"Ambos")+COUNTIFS('S8'!$B$6:$B$23,$A61,'S8'!$E$6:$E$23,"Víctor")+COUNTIFS('S8'!$B$6:$B$23,$A61,'S8'!$E$6:$E$23,"Ambos")+COUNTIFS('S9'!$B$6:$B$15,$A61,'S9'!$E$6:$E$15,"Víctor")+COUNTIFS('S9'!$B$6:$B$15,$A61,'S9'!$E$6:$E$15,"Ambos")+COUNTIFS('S10'!$B$6:$B$13,$A61,'S10'!$E$6:$E$13,"Víctor")+COUNTIFS('S10'!$B$6:$B$13,$A61,'S10'!$E$6:$E$13,"Ambos")+COUNTIFS('Holgura'!$B$6:$B$11,$A61,'Holgura'!$E$6:$E$11,"Víctor")+COUNTIFS('Holgura'!$B$6:$B$11,$A61,'Holgura'!$E$6:$E$11,"Ambos")+COUNTIFS('Entrega'!$B$6:$B$9,$A61,'Entrega'!$E$6:$E$9,"Víctor")+COUNTIFS('Entrega'!$B$6:$B$9,$A61,'Entrega'!$E$6:$E$9,"Ambos")+COUNTIFS('Defensa'!$B$6:$B$10,$A61,'Defensa'!$E$6:$E$10,"Víctor")+COUNTIFS('Defensa'!$B$6:$B$10,$A61,'Defensa'!$E$6:$E$10,"Ambos")</f>
+        <f>COUNTIFS('S1'!$B$6:$B$32,$A61,'S1'!$E$6:$E$32,"Víctor")+COUNTIFS('S1'!$B$6:$B$32,$A61,'S1'!$E$6:$E$32,"Ambos")+COUNTIFS('S2'!$B$6:$B$23,$A61,'S2'!$E$6:$E$23,"Víctor")+COUNTIFS('S2'!$B$6:$B$23,$A61,'S2'!$E$6:$E$23,"Ambos")+COUNTIFS('S3'!$B$6:$B$24,$A61,'S3'!$E$6:$E$24,"Víctor")+COUNTIFS('S3'!$B$6:$B$24,$A61,'S3'!$E$6:$E$24,"Ambos")+COUNTIFS('S4'!$B$6:$B$22,$A61,'S4'!$E$6:$E$22,"Víctor")+COUNTIFS('S4'!$B$6:$B$22,$A61,'S4'!$E$6:$E$22,"Ambos")+COUNTIFS('S5'!$B$6:$B$20,$A61,'S5'!$E$6:$E$20,"Víctor")+COUNTIFS('S5'!$B$6:$B$20,$A61,'S5'!$E$6:$E$20,"Ambos")+COUNTIFS('S6'!$B$6:$B$17,$A61,'S6'!$E$6:$E$17,"Víctor")+COUNTIFS('S6'!$B$6:$B$17,$A61,'S6'!$E$6:$E$17,"Ambos")+COUNTIFS('S7'!$B$6:$B$19,$A61,'S7'!$E$6:$E$19,"Víctor")+COUNTIFS('S7'!$B$6:$B$19,$A61,'S7'!$E$6:$E$19,"Ambos")+COUNTIFS('S8'!$B$6:$B$23,$A61,'S8'!$E$6:$E$23,"Víctor")+COUNTIFS('S8'!$B$6:$B$23,$A61,'S8'!$E$6:$E$23,"Ambos")+COUNTIFS('S9'!$B$6:$B$15,$A61,'S9'!$E$6:$E$15,"Víctor")+COUNTIFS('S9'!$B$6:$B$15,$A61,'S9'!$E$6:$E$15,"Ambos")+COUNTIFS('S10'!$B$6:$B$13,$A61,'S10'!$E$6:$E$13,"Víctor")+COUNTIFS('S10'!$B$6:$B$13,$A61,'S10'!$E$6:$E$13,"Ambos")+COUNTIFS('Holgura'!$B$6:$B$11,$A61,'Holgura'!$E$6:$E$11,"Víctor")+COUNTIFS('Holgura'!$B$6:$B$11,$A61,'Holgura'!$E$6:$E$11,"Ambos")+COUNTIFS('Entrega'!$B$6:$B$9,$A61,'Entrega'!$E$6:$E$9,"Víctor")+COUNTIFS('Entrega'!$B$6:$B$9,$A61,'Entrega'!$E$6:$E$9,"Ambos")+COUNTIFS('Defensa'!$B$6:$B$10,$A61,'Defensa'!$E$6:$E$10,"Víctor")+COUNTIFS('Defensa'!$B$6:$B$10,$A61,'Defensa'!$E$6:$E$10,"Ambos")</f>
         <v/>
       </c>
       <c r="G61" s="21">
-        <f>COUNTIFS('S1'!$B$6:$B$32,$A61,'S1'!$E$6:$E$32,"Diego")+COUNTIFS('S1'!$B$6:$B$32,$A61,'S1'!$E$6:$E$32,"Ambos")+COUNTIFS('S2'!$B$6:$B$23,$A61,'S2'!$E$6:$E$23,"Diego")+COUNTIFS('S2'!$B$6:$B$23,$A61,'S2'!$E$6:$E$23,"Ambos")+COUNTIFS('S3'!$B$6:$B$19,$A61,'S3'!$E$6:$E$19,"Diego")+COUNTIFS('S3'!$B$6:$B$19,$A61,'S3'!$E$6:$E$19,"Ambos")+COUNTIFS('S4'!$B$6:$B$20,$A61,'S4'!$E$6:$E$20,"Diego")+COUNTIFS('S4'!$B$6:$B$20,$A61,'S4'!$E$6:$E$20,"Ambos")+COUNTIFS('S5'!$B$6:$B$20,$A61,'S5'!$E$6:$E$20,"Diego")+COUNTIFS('S5'!$B$6:$B$20,$A61,'S5'!$E$6:$E$20,"Ambos")+COUNTIFS('S6'!$B$6:$B$17,$A61,'S6'!$E$6:$E$17,"Diego")+COUNTIFS('S6'!$B$6:$B$17,$A61,'S6'!$E$6:$E$17,"Ambos")+COUNTIFS('S7'!$B$6:$B$19,$A61,'S7'!$E$6:$E$19,"Diego")+COUNTIFS('S7'!$B$6:$B$19,$A61,'S7'!$E$6:$E$19,"Ambos")+COUNTIFS('S8'!$B$6:$B$23,$A61,'S8'!$E$6:$E$23,"Diego")+COUNTIFS('S8'!$B$6:$B$23,$A61,'S8'!$E$6:$E$23,"Ambos")+COUNTIFS('S9'!$B$6:$B$15,$A61,'S9'!$E$6:$E$15,"Diego")+COUNTIFS('S9'!$B$6:$B$15,$A61,'S9'!$E$6:$E$15,"Ambos")+COUNTIFS('S10'!$B$6:$B$13,$A61,'S10'!$E$6:$E$13,"Diego")+COUNTIFS('S10'!$B$6:$B$13,$A61,'S10'!$E$6:$E$13,"Ambos")+COUNTIFS('Holgura'!$B$6:$B$11,$A61,'Holgura'!$E$6:$E$11,"Diego")+COUNTIFS('Holgura'!$B$6:$B$11,$A61,'Holgura'!$E$6:$E$11,"Ambos")+COUNTIFS('Entrega'!$B$6:$B$9,$A61,'Entrega'!$E$6:$E$9,"Diego")+COUNTIFS('Entrega'!$B$6:$B$9,$A61,'Entrega'!$E$6:$E$9,"Ambos")+COUNTIFS('Defensa'!$B$6:$B$10,$A61,'Defensa'!$E$6:$E$10,"Diego")+COUNTIFS('Defensa'!$B$6:$B$10,$A61,'Defensa'!$E$6:$E$10,"Ambos")</f>
+        <f>COUNTIFS('S1'!$B$6:$B$32,$A61,'S1'!$E$6:$E$32,"Diego")+COUNTIFS('S1'!$B$6:$B$32,$A61,'S1'!$E$6:$E$32,"Ambos")+COUNTIFS('S2'!$B$6:$B$23,$A61,'S2'!$E$6:$E$23,"Diego")+COUNTIFS('S2'!$B$6:$B$23,$A61,'S2'!$E$6:$E$23,"Ambos")+COUNTIFS('S3'!$B$6:$B$24,$A61,'S3'!$E$6:$E$24,"Diego")+COUNTIFS('S3'!$B$6:$B$24,$A61,'S3'!$E$6:$E$24,"Ambos")+COUNTIFS('S4'!$B$6:$B$22,$A61,'S4'!$E$6:$E$22,"Diego")+COUNTIFS('S4'!$B$6:$B$22,$A61,'S4'!$E$6:$E$22,"Ambos")+COUNTIFS('S5'!$B$6:$B$20,$A61,'S5'!$E$6:$E$20,"Diego")+COUNTIFS('S5'!$B$6:$B$20,$A61,'S5'!$E$6:$E$20,"Ambos")+COUNTIFS('S6'!$B$6:$B$17,$A61,'S6'!$E$6:$E$17,"Diego")+COUNTIFS('S6'!$B$6:$B$17,$A61,'S6'!$E$6:$E$17,"Ambos")+COUNTIFS('S7'!$B$6:$B$19,$A61,'S7'!$E$6:$E$19,"Diego")+COUNTIFS('S7'!$B$6:$B$19,$A61,'S7'!$E$6:$E$19,"Ambos")+COUNTIFS('S8'!$B$6:$B$23,$A61,'S8'!$E$6:$E$23,"Diego")+COUNTIFS('S8'!$B$6:$B$23,$A61,'S8'!$E$6:$E$23,"Ambos")+COUNTIFS('S9'!$B$6:$B$15,$A61,'S9'!$E$6:$E$15,"Diego")+COUNTIFS('S9'!$B$6:$B$15,$A61,'S9'!$E$6:$E$15,"Ambos")+COUNTIFS('S10'!$B$6:$B$13,$A61,'S10'!$E$6:$E$13,"Diego")+COUNTIFS('S10'!$B$6:$B$13,$A61,'S10'!$E$6:$E$13,"Ambos")+COUNTIFS('Holgura'!$B$6:$B$11,$A61,'Holgura'!$E$6:$E$11,"Diego")+COUNTIFS('Holgura'!$B$6:$B$11,$A61,'Holgura'!$E$6:$E$11,"Ambos")+COUNTIFS('Entrega'!$B$6:$B$9,$A61,'Entrega'!$E$6:$E$9,"Diego")+COUNTIFS('Entrega'!$B$6:$B$9,$A61,'Entrega'!$E$6:$E$9,"Ambos")+COUNTIFS('Defensa'!$B$6:$B$10,$A61,'Defensa'!$E$6:$E$10,"Diego")+COUNTIFS('Defensa'!$B$6:$B$10,$A61,'Defensa'!$E$6:$E$10,"Ambos")</f>
         <v/>
       </c>
     </row>
@@ -10333,19 +10354,19 @@
         <v/>
       </c>
       <c r="D62" s="21">
-        <f>SUMIFS('S1'!$I$6:$I$32,'S1'!$B$6:$B$32,$A62,'S1'!$E$6:$E$32,"Víctor")+SUMIFS('S1'!$I$6:$I$32,'S1'!$B$6:$B$32,$A62,'S1'!$E$6:$E$32,"Ambos")+SUMIFS('S2'!$I$6:$I$23,'S2'!$B$6:$B$23,$A62,'S2'!$E$6:$E$23,"Víctor")+SUMIFS('S2'!$I$6:$I$23,'S2'!$B$6:$B$23,$A62,'S2'!$E$6:$E$23,"Ambos")+SUMIFS('S3'!$I$6:$I$19,'S3'!$B$6:$B$19,$A62,'S3'!$E$6:$E$19,"Víctor")+SUMIFS('S3'!$I$6:$I$19,'S3'!$B$6:$B$19,$A62,'S3'!$E$6:$E$19,"Ambos")+SUMIFS('S4'!$I$6:$I$20,'S4'!$B$6:$B$20,$A62,'S4'!$E$6:$E$20,"Víctor")+SUMIFS('S4'!$I$6:$I$20,'S4'!$B$6:$B$20,$A62,'S4'!$E$6:$E$20,"Ambos")+SUMIFS('S5'!$I$6:$I$20,'S5'!$B$6:$B$20,$A62,'S5'!$E$6:$E$20,"Víctor")+SUMIFS('S5'!$I$6:$I$20,'S5'!$B$6:$B$20,$A62,'S5'!$E$6:$E$20,"Ambos")+SUMIFS('S6'!$I$6:$I$17,'S6'!$B$6:$B$17,$A62,'S6'!$E$6:$E$17,"Víctor")+SUMIFS('S6'!$I$6:$I$17,'S6'!$B$6:$B$17,$A62,'S6'!$E$6:$E$17,"Ambos")+SUMIFS('S7'!$I$6:$I$19,'S7'!$B$6:$B$19,$A62,'S7'!$E$6:$E$19,"Víctor")+SUMIFS('S7'!$I$6:$I$19,'S7'!$B$6:$B$19,$A62,'S7'!$E$6:$E$19,"Ambos")+SUMIFS('S8'!$I$6:$I$23,'S8'!$B$6:$B$23,$A62,'S8'!$E$6:$E$23,"Víctor")+SUMIFS('S8'!$I$6:$I$23,'S8'!$B$6:$B$23,$A62,'S8'!$E$6:$E$23,"Ambos")+SUMIFS('S9'!$I$6:$I$15,'S9'!$B$6:$B$15,$A62,'S9'!$E$6:$E$15,"Víctor")+SUMIFS('S9'!$I$6:$I$15,'S9'!$B$6:$B$15,$A62,'S9'!$E$6:$E$15,"Ambos")+SUMIFS('S10'!$I$6:$I$13,'S10'!$B$6:$B$13,$A62,'S10'!$E$6:$E$13,"Víctor")+SUMIFS('S10'!$I$6:$I$13,'S10'!$B$6:$B$13,$A62,'S10'!$E$6:$E$13,"Ambos")+SUMIFS('Holgura'!$I$6:$I$11,'Holgura'!$B$6:$B$11,$A62,'Holgura'!$E$6:$E$11,"Víctor")+SUMIFS('Holgura'!$I$6:$I$11,'Holgura'!$B$6:$B$11,$A62,'Holgura'!$E$6:$E$11,"Ambos")+SUMIFS('Entrega'!$I$6:$I$9,'Entrega'!$B$6:$B$9,$A62,'Entrega'!$E$6:$E$9,"Víctor")+SUMIFS('Entrega'!$I$6:$I$9,'Entrega'!$B$6:$B$9,$A62,'Entrega'!$E$6:$E$9,"Ambos")+SUMIFS('Defensa'!$I$6:$I$10,'Defensa'!$B$6:$B$10,$A62,'Defensa'!$E$6:$E$10,"Víctor")+SUMIFS('Defensa'!$I$6:$I$10,'Defensa'!$B$6:$B$10,$A62,'Defensa'!$E$6:$E$10,"Ambos")</f>
+        <f>SUMIFS('S1'!$I$6:$I$32,'S1'!$B$6:$B$32,$A62,'S1'!$E$6:$E$32,"Víctor")+SUMIFS('S1'!$I$6:$I$32,'S1'!$B$6:$B$32,$A62,'S1'!$E$6:$E$32,"Ambos")+SUMIFS('S2'!$I$6:$I$23,'S2'!$B$6:$B$23,$A62,'S2'!$E$6:$E$23,"Víctor")+SUMIFS('S2'!$I$6:$I$23,'S2'!$B$6:$B$23,$A62,'S2'!$E$6:$E$23,"Ambos")+SUMIFS('S3'!$I$6:$I$24,'S3'!$B$6:$B$24,$A62,'S3'!$E$6:$E$24,"Víctor")+SUMIFS('S3'!$I$6:$I$24,'S3'!$B$6:$B$24,$A62,'S3'!$E$6:$E$24,"Ambos")+SUMIFS('S4'!$I$6:$I$22,'S4'!$B$6:$B$22,$A62,'S4'!$E$6:$E$22,"Víctor")+SUMIFS('S4'!$I$6:$I$22,'S4'!$B$6:$B$22,$A62,'S4'!$E$6:$E$22,"Ambos")+SUMIFS('S5'!$I$6:$I$20,'S5'!$B$6:$B$20,$A62,'S5'!$E$6:$E$20,"Víctor")+SUMIFS('S5'!$I$6:$I$20,'S5'!$B$6:$B$20,$A62,'S5'!$E$6:$E$20,"Ambos")+SUMIFS('S6'!$I$6:$I$17,'S6'!$B$6:$B$17,$A62,'S6'!$E$6:$E$17,"Víctor")+SUMIFS('S6'!$I$6:$I$17,'S6'!$B$6:$B$17,$A62,'S6'!$E$6:$E$17,"Ambos")+SUMIFS('S7'!$I$6:$I$19,'S7'!$B$6:$B$19,$A62,'S7'!$E$6:$E$19,"Víctor")+SUMIFS('S7'!$I$6:$I$19,'S7'!$B$6:$B$19,$A62,'S7'!$E$6:$E$19,"Ambos")+SUMIFS('S8'!$I$6:$I$23,'S8'!$B$6:$B$23,$A62,'S8'!$E$6:$E$23,"Víctor")+SUMIFS('S8'!$I$6:$I$23,'S8'!$B$6:$B$23,$A62,'S8'!$E$6:$E$23,"Ambos")+SUMIFS('S9'!$I$6:$I$15,'S9'!$B$6:$B$15,$A62,'S9'!$E$6:$E$15,"Víctor")+SUMIFS('S9'!$I$6:$I$15,'S9'!$B$6:$B$15,$A62,'S9'!$E$6:$E$15,"Ambos")+SUMIFS('S10'!$I$6:$I$13,'S10'!$B$6:$B$13,$A62,'S10'!$E$6:$E$13,"Víctor")+SUMIFS('S10'!$I$6:$I$13,'S10'!$B$6:$B$13,$A62,'S10'!$E$6:$E$13,"Ambos")+SUMIFS('Holgura'!$I$6:$I$11,'Holgura'!$B$6:$B$11,$A62,'Holgura'!$E$6:$E$11,"Víctor")+SUMIFS('Holgura'!$I$6:$I$11,'Holgura'!$B$6:$B$11,$A62,'Holgura'!$E$6:$E$11,"Ambos")+SUMIFS('Entrega'!$I$6:$I$9,'Entrega'!$B$6:$B$9,$A62,'Entrega'!$E$6:$E$9,"Víctor")+SUMIFS('Entrega'!$I$6:$I$9,'Entrega'!$B$6:$B$9,$A62,'Entrega'!$E$6:$E$9,"Ambos")+SUMIFS('Defensa'!$I$6:$I$10,'Defensa'!$B$6:$B$10,$A62,'Defensa'!$E$6:$E$10,"Víctor")+SUMIFS('Defensa'!$I$6:$I$10,'Defensa'!$B$6:$B$10,$A62,'Defensa'!$E$6:$E$10,"Ambos")</f>
         <v/>
       </c>
       <c r="E62" s="21">
-        <f>SUMIFS('S1'!$I$6:$I$32,'S1'!$B$6:$B$32,$A62,'S1'!$E$6:$E$32,"Diego")+SUMIFS('S1'!$I$6:$I$32,'S1'!$B$6:$B$32,$A62,'S1'!$E$6:$E$32,"Ambos")+SUMIFS('S2'!$I$6:$I$23,'S2'!$B$6:$B$23,$A62,'S2'!$E$6:$E$23,"Diego")+SUMIFS('S2'!$I$6:$I$23,'S2'!$B$6:$B$23,$A62,'S2'!$E$6:$E$23,"Ambos")+SUMIFS('S3'!$I$6:$I$19,'S3'!$B$6:$B$19,$A62,'S3'!$E$6:$E$19,"Diego")+SUMIFS('S3'!$I$6:$I$19,'S3'!$B$6:$B$19,$A62,'S3'!$E$6:$E$19,"Ambos")+SUMIFS('S4'!$I$6:$I$20,'S4'!$B$6:$B$20,$A62,'S4'!$E$6:$E$20,"Diego")+SUMIFS('S4'!$I$6:$I$20,'S4'!$B$6:$B$20,$A62,'S4'!$E$6:$E$20,"Ambos")+SUMIFS('S5'!$I$6:$I$20,'S5'!$B$6:$B$20,$A62,'S5'!$E$6:$E$20,"Diego")+SUMIFS('S5'!$I$6:$I$20,'S5'!$B$6:$B$20,$A62,'S5'!$E$6:$E$20,"Ambos")+SUMIFS('S6'!$I$6:$I$17,'S6'!$B$6:$B$17,$A62,'S6'!$E$6:$E$17,"Diego")+SUMIFS('S6'!$I$6:$I$17,'S6'!$B$6:$B$17,$A62,'S6'!$E$6:$E$17,"Ambos")+SUMIFS('S7'!$I$6:$I$19,'S7'!$B$6:$B$19,$A62,'S7'!$E$6:$E$19,"Diego")+SUMIFS('S7'!$I$6:$I$19,'S7'!$B$6:$B$19,$A62,'S7'!$E$6:$E$19,"Ambos")+SUMIFS('S8'!$I$6:$I$23,'S8'!$B$6:$B$23,$A62,'S8'!$E$6:$E$23,"Diego")+SUMIFS('S8'!$I$6:$I$23,'S8'!$B$6:$B$23,$A62,'S8'!$E$6:$E$23,"Ambos")+SUMIFS('S9'!$I$6:$I$15,'S9'!$B$6:$B$15,$A62,'S9'!$E$6:$E$15,"Diego")+SUMIFS('S9'!$I$6:$I$15,'S9'!$B$6:$B$15,$A62,'S9'!$E$6:$E$15,"Ambos")+SUMIFS('S10'!$I$6:$I$13,'S10'!$B$6:$B$13,$A62,'S10'!$E$6:$E$13,"Diego")+SUMIFS('S10'!$I$6:$I$13,'S10'!$B$6:$B$13,$A62,'S10'!$E$6:$E$13,"Ambos")+SUMIFS('Holgura'!$I$6:$I$11,'Holgura'!$B$6:$B$11,$A62,'Holgura'!$E$6:$E$11,"Diego")+SUMIFS('Holgura'!$I$6:$I$11,'Holgura'!$B$6:$B$11,$A62,'Holgura'!$E$6:$E$11,"Ambos")+SUMIFS('Entrega'!$I$6:$I$9,'Entrega'!$B$6:$B$9,$A62,'Entrega'!$E$6:$E$9,"Diego")+SUMIFS('Entrega'!$I$6:$I$9,'Entrega'!$B$6:$B$9,$A62,'Entrega'!$E$6:$E$9,"Ambos")+SUMIFS('Defensa'!$I$6:$I$10,'Defensa'!$B$6:$B$10,$A62,'Defensa'!$E$6:$E$10,"Diego")+SUMIFS('Defensa'!$I$6:$I$10,'Defensa'!$B$6:$B$10,$A62,'Defensa'!$E$6:$E$10,"Ambos")</f>
+        <f>SUMIFS('S1'!$I$6:$I$32,'S1'!$B$6:$B$32,$A62,'S1'!$E$6:$E$32,"Diego")+SUMIFS('S1'!$I$6:$I$32,'S1'!$B$6:$B$32,$A62,'S1'!$E$6:$E$32,"Ambos")+SUMIFS('S2'!$I$6:$I$23,'S2'!$B$6:$B$23,$A62,'S2'!$E$6:$E$23,"Diego")+SUMIFS('S2'!$I$6:$I$23,'S2'!$B$6:$B$23,$A62,'S2'!$E$6:$E$23,"Ambos")+SUMIFS('S3'!$I$6:$I$24,'S3'!$B$6:$B$24,$A62,'S3'!$E$6:$E$24,"Diego")+SUMIFS('S3'!$I$6:$I$24,'S3'!$B$6:$B$24,$A62,'S3'!$E$6:$E$24,"Ambos")+SUMIFS('S4'!$I$6:$I$22,'S4'!$B$6:$B$22,$A62,'S4'!$E$6:$E$22,"Diego")+SUMIFS('S4'!$I$6:$I$22,'S4'!$B$6:$B$22,$A62,'S4'!$E$6:$E$22,"Ambos")+SUMIFS('S5'!$I$6:$I$20,'S5'!$B$6:$B$20,$A62,'S5'!$E$6:$E$20,"Diego")+SUMIFS('S5'!$I$6:$I$20,'S5'!$B$6:$B$20,$A62,'S5'!$E$6:$E$20,"Ambos")+SUMIFS('S6'!$I$6:$I$17,'S6'!$B$6:$B$17,$A62,'S6'!$E$6:$E$17,"Diego")+SUMIFS('S6'!$I$6:$I$17,'S6'!$B$6:$B$17,$A62,'S6'!$E$6:$E$17,"Ambos")+SUMIFS('S7'!$I$6:$I$19,'S7'!$B$6:$B$19,$A62,'S7'!$E$6:$E$19,"Diego")+SUMIFS('S7'!$I$6:$I$19,'S7'!$B$6:$B$19,$A62,'S7'!$E$6:$E$19,"Ambos")+SUMIFS('S8'!$I$6:$I$23,'S8'!$B$6:$B$23,$A62,'S8'!$E$6:$E$23,"Diego")+SUMIFS('S8'!$I$6:$I$23,'S8'!$B$6:$B$23,$A62,'S8'!$E$6:$E$23,"Ambos")+SUMIFS('S9'!$I$6:$I$15,'S9'!$B$6:$B$15,$A62,'S9'!$E$6:$E$15,"Diego")+SUMIFS('S9'!$I$6:$I$15,'S9'!$B$6:$B$15,$A62,'S9'!$E$6:$E$15,"Ambos")+SUMIFS('S10'!$I$6:$I$13,'S10'!$B$6:$B$13,$A62,'S10'!$E$6:$E$13,"Diego")+SUMIFS('S10'!$I$6:$I$13,'S10'!$B$6:$B$13,$A62,'S10'!$E$6:$E$13,"Ambos")+SUMIFS('Holgura'!$I$6:$I$11,'Holgura'!$B$6:$B$11,$A62,'Holgura'!$E$6:$E$11,"Diego")+SUMIFS('Holgura'!$I$6:$I$11,'Holgura'!$B$6:$B$11,$A62,'Holgura'!$E$6:$E$11,"Ambos")+SUMIFS('Entrega'!$I$6:$I$9,'Entrega'!$B$6:$B$9,$A62,'Entrega'!$E$6:$E$9,"Diego")+SUMIFS('Entrega'!$I$6:$I$9,'Entrega'!$B$6:$B$9,$A62,'Entrega'!$E$6:$E$9,"Ambos")+SUMIFS('Defensa'!$I$6:$I$10,'Defensa'!$B$6:$B$10,$A62,'Defensa'!$E$6:$E$10,"Diego")+SUMIFS('Defensa'!$I$6:$I$10,'Defensa'!$B$6:$B$10,$A62,'Defensa'!$E$6:$E$10,"Ambos")</f>
         <v/>
       </c>
       <c r="F62" s="21">
-        <f>COUNTIFS('S1'!$B$6:$B$32,$A62,'S1'!$E$6:$E$32,"Víctor")+COUNTIFS('S1'!$B$6:$B$32,$A62,'S1'!$E$6:$E$32,"Ambos")+COUNTIFS('S2'!$B$6:$B$23,$A62,'S2'!$E$6:$E$23,"Víctor")+COUNTIFS('S2'!$B$6:$B$23,$A62,'S2'!$E$6:$E$23,"Ambos")+COUNTIFS('S3'!$B$6:$B$19,$A62,'S3'!$E$6:$E$19,"Víctor")+COUNTIFS('S3'!$B$6:$B$19,$A62,'S3'!$E$6:$E$19,"Ambos")+COUNTIFS('S4'!$B$6:$B$20,$A62,'S4'!$E$6:$E$20,"Víctor")+COUNTIFS('S4'!$B$6:$B$20,$A62,'S4'!$E$6:$E$20,"Ambos")+COUNTIFS('S5'!$B$6:$B$20,$A62,'S5'!$E$6:$E$20,"Víctor")+COUNTIFS('S5'!$B$6:$B$20,$A62,'S5'!$E$6:$E$20,"Ambos")+COUNTIFS('S6'!$B$6:$B$17,$A62,'S6'!$E$6:$E$17,"Víctor")+COUNTIFS('S6'!$B$6:$B$17,$A62,'S6'!$E$6:$E$17,"Ambos")+COUNTIFS('S7'!$B$6:$B$19,$A62,'S7'!$E$6:$E$19,"Víctor")+COUNTIFS('S7'!$B$6:$B$19,$A62,'S7'!$E$6:$E$19,"Ambos")+COUNTIFS('S8'!$B$6:$B$23,$A62,'S8'!$E$6:$E$23,"Víctor")+COUNTIFS('S8'!$B$6:$B$23,$A62,'S8'!$E$6:$E$23,"Ambos")+COUNTIFS('S9'!$B$6:$B$15,$A62,'S9'!$E$6:$E$15,"Víctor")+COUNTIFS('S9'!$B$6:$B$15,$A62,'S9'!$E$6:$E$15,"Ambos")+COUNTIFS('S10'!$B$6:$B$13,$A62,'S10'!$E$6:$E$13,"Víctor")+COUNTIFS('S10'!$B$6:$B$13,$A62,'S10'!$E$6:$E$13,"Ambos")+COUNTIFS('Holgura'!$B$6:$B$11,$A62,'Holgura'!$E$6:$E$11,"Víctor")+COUNTIFS('Holgura'!$B$6:$B$11,$A62,'Holgura'!$E$6:$E$11,"Ambos")+COUNTIFS('Entrega'!$B$6:$B$9,$A62,'Entrega'!$E$6:$E$9,"Víctor")+COUNTIFS('Entrega'!$B$6:$B$9,$A62,'Entrega'!$E$6:$E$9,"Ambos")+COUNTIFS('Defensa'!$B$6:$B$10,$A62,'Defensa'!$E$6:$E$10,"Víctor")+COUNTIFS('Defensa'!$B$6:$B$10,$A62,'Defensa'!$E$6:$E$10,"Ambos")</f>
+        <f>COUNTIFS('S1'!$B$6:$B$32,$A62,'S1'!$E$6:$E$32,"Víctor")+COUNTIFS('S1'!$B$6:$B$32,$A62,'S1'!$E$6:$E$32,"Ambos")+COUNTIFS('S2'!$B$6:$B$23,$A62,'S2'!$E$6:$E$23,"Víctor")+COUNTIFS('S2'!$B$6:$B$23,$A62,'S2'!$E$6:$E$23,"Ambos")+COUNTIFS('S3'!$B$6:$B$24,$A62,'S3'!$E$6:$E$24,"Víctor")+COUNTIFS('S3'!$B$6:$B$24,$A62,'S3'!$E$6:$E$24,"Ambos")+COUNTIFS('S4'!$B$6:$B$22,$A62,'S4'!$E$6:$E$22,"Víctor")+COUNTIFS('S4'!$B$6:$B$22,$A62,'S4'!$E$6:$E$22,"Ambos")+COUNTIFS('S5'!$B$6:$B$20,$A62,'S5'!$E$6:$E$20,"Víctor")+COUNTIFS('S5'!$B$6:$B$20,$A62,'S5'!$E$6:$E$20,"Ambos")+COUNTIFS('S6'!$B$6:$B$17,$A62,'S6'!$E$6:$E$17,"Víctor")+COUNTIFS('S6'!$B$6:$B$17,$A62,'S6'!$E$6:$E$17,"Ambos")+COUNTIFS('S7'!$B$6:$B$19,$A62,'S7'!$E$6:$E$19,"Víctor")+COUNTIFS('S7'!$B$6:$B$19,$A62,'S7'!$E$6:$E$19,"Ambos")+COUNTIFS('S8'!$B$6:$B$23,$A62,'S8'!$E$6:$E$23,"Víctor")+COUNTIFS('S8'!$B$6:$B$23,$A62,'S8'!$E$6:$E$23,"Ambos")+COUNTIFS('S9'!$B$6:$B$15,$A62,'S9'!$E$6:$E$15,"Víctor")+COUNTIFS('S9'!$B$6:$B$15,$A62,'S9'!$E$6:$E$15,"Ambos")+COUNTIFS('S10'!$B$6:$B$13,$A62,'S10'!$E$6:$E$13,"Víctor")+COUNTIFS('S10'!$B$6:$B$13,$A62,'S10'!$E$6:$E$13,"Ambos")+COUNTIFS('Holgura'!$B$6:$B$11,$A62,'Holgura'!$E$6:$E$11,"Víctor")+COUNTIFS('Holgura'!$B$6:$B$11,$A62,'Holgura'!$E$6:$E$11,"Ambos")+COUNTIFS('Entrega'!$B$6:$B$9,$A62,'Entrega'!$E$6:$E$9,"Víctor")+COUNTIFS('Entrega'!$B$6:$B$9,$A62,'Entrega'!$E$6:$E$9,"Ambos")+COUNTIFS('Defensa'!$B$6:$B$10,$A62,'Defensa'!$E$6:$E$10,"Víctor")+COUNTIFS('Defensa'!$B$6:$B$10,$A62,'Defensa'!$E$6:$E$10,"Ambos")</f>
         <v/>
       </c>
       <c r="G62" s="21">
-        <f>COUNTIFS('S1'!$B$6:$B$32,$A62,'S1'!$E$6:$E$32,"Diego")+COUNTIFS('S1'!$B$6:$B$32,$A62,'S1'!$E$6:$E$32,"Ambos")+COUNTIFS('S2'!$B$6:$B$23,$A62,'S2'!$E$6:$E$23,"Diego")+COUNTIFS('S2'!$B$6:$B$23,$A62,'S2'!$E$6:$E$23,"Ambos")+COUNTIFS('S3'!$B$6:$B$19,$A62,'S3'!$E$6:$E$19,"Diego")+COUNTIFS('S3'!$B$6:$B$19,$A62,'S3'!$E$6:$E$19,"Ambos")+COUNTIFS('S4'!$B$6:$B$20,$A62,'S4'!$E$6:$E$20,"Diego")+COUNTIFS('S4'!$B$6:$B$20,$A62,'S4'!$E$6:$E$20,"Ambos")+COUNTIFS('S5'!$B$6:$B$20,$A62,'S5'!$E$6:$E$20,"Diego")+COUNTIFS('S5'!$B$6:$B$20,$A62,'S5'!$E$6:$E$20,"Ambos")+COUNTIFS('S6'!$B$6:$B$17,$A62,'S6'!$E$6:$E$17,"Diego")+COUNTIFS('S6'!$B$6:$B$17,$A62,'S6'!$E$6:$E$17,"Ambos")+COUNTIFS('S7'!$B$6:$B$19,$A62,'S7'!$E$6:$E$19,"Diego")+COUNTIFS('S7'!$B$6:$B$19,$A62,'S7'!$E$6:$E$19,"Ambos")+COUNTIFS('S8'!$B$6:$B$23,$A62,'S8'!$E$6:$E$23,"Diego")+COUNTIFS('S8'!$B$6:$B$23,$A62,'S8'!$E$6:$E$23,"Ambos")+COUNTIFS('S9'!$B$6:$B$15,$A62,'S9'!$E$6:$E$15,"Diego")+COUNTIFS('S9'!$B$6:$B$15,$A62,'S9'!$E$6:$E$15,"Ambos")+COUNTIFS('S10'!$B$6:$B$13,$A62,'S10'!$E$6:$E$13,"Diego")+COUNTIFS('S10'!$B$6:$B$13,$A62,'S10'!$E$6:$E$13,"Ambos")+COUNTIFS('Holgura'!$B$6:$B$11,$A62,'Holgura'!$E$6:$E$11,"Diego")+COUNTIFS('Holgura'!$B$6:$B$11,$A62,'Holgura'!$E$6:$E$11,"Ambos")+COUNTIFS('Entrega'!$B$6:$B$9,$A62,'Entrega'!$E$6:$E$9,"Diego")+COUNTIFS('Entrega'!$B$6:$B$9,$A62,'Entrega'!$E$6:$E$9,"Ambos")+COUNTIFS('Defensa'!$B$6:$B$10,$A62,'Defensa'!$E$6:$E$10,"Diego")+COUNTIFS('Defensa'!$B$6:$B$10,$A62,'Defensa'!$E$6:$E$10,"Ambos")</f>
+        <f>COUNTIFS('S1'!$B$6:$B$32,$A62,'S1'!$E$6:$E$32,"Diego")+COUNTIFS('S1'!$B$6:$B$32,$A62,'S1'!$E$6:$E$32,"Ambos")+COUNTIFS('S2'!$B$6:$B$23,$A62,'S2'!$E$6:$E$23,"Diego")+COUNTIFS('S2'!$B$6:$B$23,$A62,'S2'!$E$6:$E$23,"Ambos")+COUNTIFS('S3'!$B$6:$B$24,$A62,'S3'!$E$6:$E$24,"Diego")+COUNTIFS('S3'!$B$6:$B$24,$A62,'S3'!$E$6:$E$24,"Ambos")+COUNTIFS('S4'!$B$6:$B$22,$A62,'S4'!$E$6:$E$22,"Diego")+COUNTIFS('S4'!$B$6:$B$22,$A62,'S4'!$E$6:$E$22,"Ambos")+COUNTIFS('S5'!$B$6:$B$20,$A62,'S5'!$E$6:$E$20,"Diego")+COUNTIFS('S5'!$B$6:$B$20,$A62,'S5'!$E$6:$E$20,"Ambos")+COUNTIFS('S6'!$B$6:$B$17,$A62,'S6'!$E$6:$E$17,"Diego")+COUNTIFS('S6'!$B$6:$B$17,$A62,'S6'!$E$6:$E$17,"Ambos")+COUNTIFS('S7'!$B$6:$B$19,$A62,'S7'!$E$6:$E$19,"Diego")+COUNTIFS('S7'!$B$6:$B$19,$A62,'S7'!$E$6:$E$19,"Ambos")+COUNTIFS('S8'!$B$6:$B$23,$A62,'S8'!$E$6:$E$23,"Diego")+COUNTIFS('S8'!$B$6:$B$23,$A62,'S8'!$E$6:$E$23,"Ambos")+COUNTIFS('S9'!$B$6:$B$15,$A62,'S9'!$E$6:$E$15,"Diego")+COUNTIFS('S9'!$B$6:$B$15,$A62,'S9'!$E$6:$E$15,"Ambos")+COUNTIFS('S10'!$B$6:$B$13,$A62,'S10'!$E$6:$E$13,"Diego")+COUNTIFS('S10'!$B$6:$B$13,$A62,'S10'!$E$6:$E$13,"Ambos")+COUNTIFS('Holgura'!$B$6:$B$11,$A62,'Holgura'!$E$6:$E$11,"Diego")+COUNTIFS('Holgura'!$B$6:$B$11,$A62,'Holgura'!$E$6:$E$11,"Ambos")+COUNTIFS('Entrega'!$B$6:$B$9,$A62,'Entrega'!$E$6:$E$9,"Diego")+COUNTIFS('Entrega'!$B$6:$B$9,$A62,'Entrega'!$E$6:$E$9,"Ambos")+COUNTIFS('Defensa'!$B$6:$B$10,$A62,'Defensa'!$E$6:$E$10,"Diego")+COUNTIFS('Defensa'!$B$6:$B$10,$A62,'Defensa'!$E$6:$E$10,"Ambos")</f>
         <v/>
       </c>
     </row>
@@ -10362,19 +10383,19 @@
         <v/>
       </c>
       <c r="D63" s="21">
-        <f>SUMIFS('S1'!$I$6:$I$32,'S1'!$B$6:$B$32,$A63,'S1'!$E$6:$E$32,"Víctor")+SUMIFS('S1'!$I$6:$I$32,'S1'!$B$6:$B$32,$A63,'S1'!$E$6:$E$32,"Ambos")+SUMIFS('S2'!$I$6:$I$23,'S2'!$B$6:$B$23,$A63,'S2'!$E$6:$E$23,"Víctor")+SUMIFS('S2'!$I$6:$I$23,'S2'!$B$6:$B$23,$A63,'S2'!$E$6:$E$23,"Ambos")+SUMIFS('S3'!$I$6:$I$19,'S3'!$B$6:$B$19,$A63,'S3'!$E$6:$E$19,"Víctor")+SUMIFS('S3'!$I$6:$I$19,'S3'!$B$6:$B$19,$A63,'S3'!$E$6:$E$19,"Ambos")+SUMIFS('S4'!$I$6:$I$20,'S4'!$B$6:$B$20,$A63,'S4'!$E$6:$E$20,"Víctor")+SUMIFS('S4'!$I$6:$I$20,'S4'!$B$6:$B$20,$A63,'S4'!$E$6:$E$20,"Ambos")+SUMIFS('S5'!$I$6:$I$20,'S5'!$B$6:$B$20,$A63,'S5'!$E$6:$E$20,"Víctor")+SUMIFS('S5'!$I$6:$I$20,'S5'!$B$6:$B$20,$A63,'S5'!$E$6:$E$20,"Ambos")+SUMIFS('S6'!$I$6:$I$17,'S6'!$B$6:$B$17,$A63,'S6'!$E$6:$E$17,"Víctor")+SUMIFS('S6'!$I$6:$I$17,'S6'!$B$6:$B$17,$A63,'S6'!$E$6:$E$17,"Ambos")+SUMIFS('S7'!$I$6:$I$19,'S7'!$B$6:$B$19,$A63,'S7'!$E$6:$E$19,"Víctor")+SUMIFS('S7'!$I$6:$I$19,'S7'!$B$6:$B$19,$A63,'S7'!$E$6:$E$19,"Ambos")+SUMIFS('S8'!$I$6:$I$23,'S8'!$B$6:$B$23,$A63,'S8'!$E$6:$E$23,"Víctor")+SUMIFS('S8'!$I$6:$I$23,'S8'!$B$6:$B$23,$A63,'S8'!$E$6:$E$23,"Ambos")+SUMIFS('S9'!$I$6:$I$15,'S9'!$B$6:$B$15,$A63,'S9'!$E$6:$E$15,"Víctor")+SUMIFS('S9'!$I$6:$I$15,'S9'!$B$6:$B$15,$A63,'S9'!$E$6:$E$15,"Ambos")+SUMIFS('S10'!$I$6:$I$13,'S10'!$B$6:$B$13,$A63,'S10'!$E$6:$E$13,"Víctor")+SUMIFS('S10'!$I$6:$I$13,'S10'!$B$6:$B$13,$A63,'S10'!$E$6:$E$13,"Ambos")+SUMIFS('Holgura'!$I$6:$I$11,'Holgura'!$B$6:$B$11,$A63,'Holgura'!$E$6:$E$11,"Víctor")+SUMIFS('Holgura'!$I$6:$I$11,'Holgura'!$B$6:$B$11,$A63,'Holgura'!$E$6:$E$11,"Ambos")+SUMIFS('Entrega'!$I$6:$I$9,'Entrega'!$B$6:$B$9,$A63,'Entrega'!$E$6:$E$9,"Víctor")+SUMIFS('Entrega'!$I$6:$I$9,'Entrega'!$B$6:$B$9,$A63,'Entrega'!$E$6:$E$9,"Ambos")+SUMIFS('Defensa'!$I$6:$I$10,'Defensa'!$B$6:$B$10,$A63,'Defensa'!$E$6:$E$10,"Víctor")+SUMIFS('Defensa'!$I$6:$I$10,'Defensa'!$B$6:$B$10,$A63,'Defensa'!$E$6:$E$10,"Ambos")</f>
+        <f>SUMIFS('S1'!$I$6:$I$32,'S1'!$B$6:$B$32,$A63,'S1'!$E$6:$E$32,"Víctor")+SUMIFS('S1'!$I$6:$I$32,'S1'!$B$6:$B$32,$A63,'S1'!$E$6:$E$32,"Ambos")+SUMIFS('S2'!$I$6:$I$23,'S2'!$B$6:$B$23,$A63,'S2'!$E$6:$E$23,"Víctor")+SUMIFS('S2'!$I$6:$I$23,'S2'!$B$6:$B$23,$A63,'S2'!$E$6:$E$23,"Ambos")+SUMIFS('S3'!$I$6:$I$24,'S3'!$B$6:$B$24,$A63,'S3'!$E$6:$E$24,"Víctor")+SUMIFS('S3'!$I$6:$I$24,'S3'!$B$6:$B$24,$A63,'S3'!$E$6:$E$24,"Ambos")+SUMIFS('S4'!$I$6:$I$22,'S4'!$B$6:$B$22,$A63,'S4'!$E$6:$E$22,"Víctor")+SUMIFS('S4'!$I$6:$I$22,'S4'!$B$6:$B$22,$A63,'S4'!$E$6:$E$22,"Ambos")+SUMIFS('S5'!$I$6:$I$20,'S5'!$B$6:$B$20,$A63,'S5'!$E$6:$E$20,"Víctor")+SUMIFS('S5'!$I$6:$I$20,'S5'!$B$6:$B$20,$A63,'S5'!$E$6:$E$20,"Ambos")+SUMIFS('S6'!$I$6:$I$17,'S6'!$B$6:$B$17,$A63,'S6'!$E$6:$E$17,"Víctor")+SUMIFS('S6'!$I$6:$I$17,'S6'!$B$6:$B$17,$A63,'S6'!$E$6:$E$17,"Ambos")+SUMIFS('S7'!$I$6:$I$19,'S7'!$B$6:$B$19,$A63,'S7'!$E$6:$E$19,"Víctor")+SUMIFS('S7'!$I$6:$I$19,'S7'!$B$6:$B$19,$A63,'S7'!$E$6:$E$19,"Ambos")+SUMIFS('S8'!$I$6:$I$23,'S8'!$B$6:$B$23,$A63,'S8'!$E$6:$E$23,"Víctor")+SUMIFS('S8'!$I$6:$I$23,'S8'!$B$6:$B$23,$A63,'S8'!$E$6:$E$23,"Ambos")+SUMIFS('S9'!$I$6:$I$15,'S9'!$B$6:$B$15,$A63,'S9'!$E$6:$E$15,"Víctor")+SUMIFS('S9'!$I$6:$I$15,'S9'!$B$6:$B$15,$A63,'S9'!$E$6:$E$15,"Ambos")+SUMIFS('S10'!$I$6:$I$13,'S10'!$B$6:$B$13,$A63,'S10'!$E$6:$E$13,"Víctor")+SUMIFS('S10'!$I$6:$I$13,'S10'!$B$6:$B$13,$A63,'S10'!$E$6:$E$13,"Ambos")+SUMIFS('Holgura'!$I$6:$I$11,'Holgura'!$B$6:$B$11,$A63,'Holgura'!$E$6:$E$11,"Víctor")+SUMIFS('Holgura'!$I$6:$I$11,'Holgura'!$B$6:$B$11,$A63,'Holgura'!$E$6:$E$11,"Ambos")+SUMIFS('Entrega'!$I$6:$I$9,'Entrega'!$B$6:$B$9,$A63,'Entrega'!$E$6:$E$9,"Víctor")+SUMIFS('Entrega'!$I$6:$I$9,'Entrega'!$B$6:$B$9,$A63,'Entrega'!$E$6:$E$9,"Ambos")+SUMIFS('Defensa'!$I$6:$I$10,'Defensa'!$B$6:$B$10,$A63,'Defensa'!$E$6:$E$10,"Víctor")+SUMIFS('Defensa'!$I$6:$I$10,'Defensa'!$B$6:$B$10,$A63,'Defensa'!$E$6:$E$10,"Ambos")</f>
         <v/>
       </c>
       <c r="E63" s="21">
-        <f>SUMIFS('S1'!$I$6:$I$32,'S1'!$B$6:$B$32,$A63,'S1'!$E$6:$E$32,"Diego")+SUMIFS('S1'!$I$6:$I$32,'S1'!$B$6:$B$32,$A63,'S1'!$E$6:$E$32,"Ambos")+SUMIFS('S2'!$I$6:$I$23,'S2'!$B$6:$B$23,$A63,'S2'!$E$6:$E$23,"Diego")+SUMIFS('S2'!$I$6:$I$23,'S2'!$B$6:$B$23,$A63,'S2'!$E$6:$E$23,"Ambos")+SUMIFS('S3'!$I$6:$I$19,'S3'!$B$6:$B$19,$A63,'S3'!$E$6:$E$19,"Diego")+SUMIFS('S3'!$I$6:$I$19,'S3'!$B$6:$B$19,$A63,'S3'!$E$6:$E$19,"Ambos")+SUMIFS('S4'!$I$6:$I$20,'S4'!$B$6:$B$20,$A63,'S4'!$E$6:$E$20,"Diego")+SUMIFS('S4'!$I$6:$I$20,'S4'!$B$6:$B$20,$A63,'S4'!$E$6:$E$20,"Ambos")+SUMIFS('S5'!$I$6:$I$20,'S5'!$B$6:$B$20,$A63,'S5'!$E$6:$E$20,"Diego")+SUMIFS('S5'!$I$6:$I$20,'S5'!$B$6:$B$20,$A63,'S5'!$E$6:$E$20,"Ambos")+SUMIFS('S6'!$I$6:$I$17,'S6'!$B$6:$B$17,$A63,'S6'!$E$6:$E$17,"Diego")+SUMIFS('S6'!$I$6:$I$17,'S6'!$B$6:$B$17,$A63,'S6'!$E$6:$E$17,"Ambos")+SUMIFS('S7'!$I$6:$I$19,'S7'!$B$6:$B$19,$A63,'S7'!$E$6:$E$19,"Diego")+SUMIFS('S7'!$I$6:$I$19,'S7'!$B$6:$B$19,$A63,'S7'!$E$6:$E$19,"Ambos")+SUMIFS('S8'!$I$6:$I$23,'S8'!$B$6:$B$23,$A63,'S8'!$E$6:$E$23,"Diego")+SUMIFS('S8'!$I$6:$I$23,'S8'!$B$6:$B$23,$A63,'S8'!$E$6:$E$23,"Ambos")+SUMIFS('S9'!$I$6:$I$15,'S9'!$B$6:$B$15,$A63,'S9'!$E$6:$E$15,"Diego")+SUMIFS('S9'!$I$6:$I$15,'S9'!$B$6:$B$15,$A63,'S9'!$E$6:$E$15,"Ambos")+SUMIFS('S10'!$I$6:$I$13,'S10'!$B$6:$B$13,$A63,'S10'!$E$6:$E$13,"Diego")+SUMIFS('S10'!$I$6:$I$13,'S10'!$B$6:$B$13,$A63,'S10'!$E$6:$E$13,"Ambos")+SUMIFS('Holgura'!$I$6:$I$11,'Holgura'!$B$6:$B$11,$A63,'Holgura'!$E$6:$E$11,"Diego")+SUMIFS('Holgura'!$I$6:$I$11,'Holgura'!$B$6:$B$11,$A63,'Holgura'!$E$6:$E$11,"Ambos")+SUMIFS('Entrega'!$I$6:$I$9,'Entrega'!$B$6:$B$9,$A63,'Entrega'!$E$6:$E$9,"Diego")+SUMIFS('Entrega'!$I$6:$I$9,'Entrega'!$B$6:$B$9,$A63,'Entrega'!$E$6:$E$9,"Ambos")+SUMIFS('Defensa'!$I$6:$I$10,'Defensa'!$B$6:$B$10,$A63,'Defensa'!$E$6:$E$10,"Diego")+SUMIFS('Defensa'!$I$6:$I$10,'Defensa'!$B$6:$B$10,$A63,'Defensa'!$E$6:$E$10,"Ambos")</f>
+        <f>SUMIFS('S1'!$I$6:$I$32,'S1'!$B$6:$B$32,$A63,'S1'!$E$6:$E$32,"Diego")+SUMIFS('S1'!$I$6:$I$32,'S1'!$B$6:$B$32,$A63,'S1'!$E$6:$E$32,"Ambos")+SUMIFS('S2'!$I$6:$I$23,'S2'!$B$6:$B$23,$A63,'S2'!$E$6:$E$23,"Diego")+SUMIFS('S2'!$I$6:$I$23,'S2'!$B$6:$B$23,$A63,'S2'!$E$6:$E$23,"Ambos")+SUMIFS('S3'!$I$6:$I$24,'S3'!$B$6:$B$24,$A63,'S3'!$E$6:$E$24,"Diego")+SUMIFS('S3'!$I$6:$I$24,'S3'!$B$6:$B$24,$A63,'S3'!$E$6:$E$24,"Ambos")+SUMIFS('S4'!$I$6:$I$22,'S4'!$B$6:$B$22,$A63,'S4'!$E$6:$E$22,"Diego")+SUMIFS('S4'!$I$6:$I$22,'S4'!$B$6:$B$22,$A63,'S4'!$E$6:$E$22,"Ambos")+SUMIFS('S5'!$I$6:$I$20,'S5'!$B$6:$B$20,$A63,'S5'!$E$6:$E$20,"Diego")+SUMIFS('S5'!$I$6:$I$20,'S5'!$B$6:$B$20,$A63,'S5'!$E$6:$E$20,"Ambos")+SUMIFS('S6'!$I$6:$I$17,'S6'!$B$6:$B$17,$A63,'S6'!$E$6:$E$17,"Diego")+SUMIFS('S6'!$I$6:$I$17,'S6'!$B$6:$B$17,$A63,'S6'!$E$6:$E$17,"Ambos")+SUMIFS('S7'!$I$6:$I$19,'S7'!$B$6:$B$19,$A63,'S7'!$E$6:$E$19,"Diego")+SUMIFS('S7'!$I$6:$I$19,'S7'!$B$6:$B$19,$A63,'S7'!$E$6:$E$19,"Ambos")+SUMIFS('S8'!$I$6:$I$23,'S8'!$B$6:$B$23,$A63,'S8'!$E$6:$E$23,"Diego")+SUMIFS('S8'!$I$6:$I$23,'S8'!$B$6:$B$23,$A63,'S8'!$E$6:$E$23,"Ambos")+SUMIFS('S9'!$I$6:$I$15,'S9'!$B$6:$B$15,$A63,'S9'!$E$6:$E$15,"Diego")+SUMIFS('S9'!$I$6:$I$15,'S9'!$B$6:$B$15,$A63,'S9'!$E$6:$E$15,"Ambos")+SUMIFS('S10'!$I$6:$I$13,'S10'!$B$6:$B$13,$A63,'S10'!$E$6:$E$13,"Diego")+SUMIFS('S10'!$I$6:$I$13,'S10'!$B$6:$B$13,$A63,'S10'!$E$6:$E$13,"Ambos")+SUMIFS('Holgura'!$I$6:$I$11,'Holgura'!$B$6:$B$11,$A63,'Holgura'!$E$6:$E$11,"Diego")+SUMIFS('Holgura'!$I$6:$I$11,'Holgura'!$B$6:$B$11,$A63,'Holgura'!$E$6:$E$11,"Ambos")+SUMIFS('Entrega'!$I$6:$I$9,'Entrega'!$B$6:$B$9,$A63,'Entrega'!$E$6:$E$9,"Diego")+SUMIFS('Entrega'!$I$6:$I$9,'Entrega'!$B$6:$B$9,$A63,'Entrega'!$E$6:$E$9,"Ambos")+SUMIFS('Defensa'!$I$6:$I$10,'Defensa'!$B$6:$B$10,$A63,'Defensa'!$E$6:$E$10,"Diego")+SUMIFS('Defensa'!$I$6:$I$10,'Defensa'!$B$6:$B$10,$A63,'Defensa'!$E$6:$E$10,"Ambos")</f>
         <v/>
       </c>
       <c r="F63" s="21">
-        <f>COUNTIFS('S1'!$B$6:$B$32,$A63,'S1'!$E$6:$E$32,"Víctor")+COUNTIFS('S1'!$B$6:$B$32,$A63,'S1'!$E$6:$E$32,"Ambos")+COUNTIFS('S2'!$B$6:$B$23,$A63,'S2'!$E$6:$E$23,"Víctor")+COUNTIFS('S2'!$B$6:$B$23,$A63,'S2'!$E$6:$E$23,"Ambos")+COUNTIFS('S3'!$B$6:$B$19,$A63,'S3'!$E$6:$E$19,"Víctor")+COUNTIFS('S3'!$B$6:$B$19,$A63,'S3'!$E$6:$E$19,"Ambos")+COUNTIFS('S4'!$B$6:$B$20,$A63,'S4'!$E$6:$E$20,"Víctor")+COUNTIFS('S4'!$B$6:$B$20,$A63,'S4'!$E$6:$E$20,"Ambos")+COUNTIFS('S5'!$B$6:$B$20,$A63,'S5'!$E$6:$E$20,"Víctor")+COUNTIFS('S5'!$B$6:$B$20,$A63,'S5'!$E$6:$E$20,"Ambos")+COUNTIFS('S6'!$B$6:$B$17,$A63,'S6'!$E$6:$E$17,"Víctor")+COUNTIFS('S6'!$B$6:$B$17,$A63,'S6'!$E$6:$E$17,"Ambos")+COUNTIFS('S7'!$B$6:$B$19,$A63,'S7'!$E$6:$E$19,"Víctor")+COUNTIFS('S7'!$B$6:$B$19,$A63,'S7'!$E$6:$E$19,"Ambos")+COUNTIFS('S8'!$B$6:$B$23,$A63,'S8'!$E$6:$E$23,"Víctor")+COUNTIFS('S8'!$B$6:$B$23,$A63,'S8'!$E$6:$E$23,"Ambos")+COUNTIFS('S9'!$B$6:$B$15,$A63,'S9'!$E$6:$E$15,"Víctor")+COUNTIFS('S9'!$B$6:$B$15,$A63,'S9'!$E$6:$E$15,"Ambos")+COUNTIFS('S10'!$B$6:$B$13,$A63,'S10'!$E$6:$E$13,"Víctor")+COUNTIFS('S10'!$B$6:$B$13,$A63,'S10'!$E$6:$E$13,"Ambos")+COUNTIFS('Holgura'!$B$6:$B$11,$A63,'Holgura'!$E$6:$E$11,"Víctor")+COUNTIFS('Holgura'!$B$6:$B$11,$A63,'Holgura'!$E$6:$E$11,"Ambos")+COUNTIFS('Entrega'!$B$6:$B$9,$A63,'Entrega'!$E$6:$E$9,"Víctor")+COUNTIFS('Entrega'!$B$6:$B$9,$A63,'Entrega'!$E$6:$E$9,"Ambos")+COUNTIFS('Defensa'!$B$6:$B$10,$A63,'Defensa'!$E$6:$E$10,"Víctor")+COUNTIFS('Defensa'!$B$6:$B$10,$A63,'Defensa'!$E$6:$E$10,"Ambos")</f>
+        <f>COUNTIFS('S1'!$B$6:$B$32,$A63,'S1'!$E$6:$E$32,"Víctor")+COUNTIFS('S1'!$B$6:$B$32,$A63,'S1'!$E$6:$E$32,"Ambos")+COUNTIFS('S2'!$B$6:$B$23,$A63,'S2'!$E$6:$E$23,"Víctor")+COUNTIFS('S2'!$B$6:$B$23,$A63,'S2'!$E$6:$E$23,"Ambos")+COUNTIFS('S3'!$B$6:$B$24,$A63,'S3'!$E$6:$E$24,"Víctor")+COUNTIFS('S3'!$B$6:$B$24,$A63,'S3'!$E$6:$E$24,"Ambos")+COUNTIFS('S4'!$B$6:$B$22,$A63,'S4'!$E$6:$E$22,"Víctor")+COUNTIFS('S4'!$B$6:$B$22,$A63,'S4'!$E$6:$E$22,"Ambos")+COUNTIFS('S5'!$B$6:$B$20,$A63,'S5'!$E$6:$E$20,"Víctor")+COUNTIFS('S5'!$B$6:$B$20,$A63,'S5'!$E$6:$E$20,"Ambos")+COUNTIFS('S6'!$B$6:$B$17,$A63,'S6'!$E$6:$E$17,"Víctor")+COUNTIFS('S6'!$B$6:$B$17,$A63,'S6'!$E$6:$E$17,"Ambos")+COUNTIFS('S7'!$B$6:$B$19,$A63,'S7'!$E$6:$E$19,"Víctor")+COUNTIFS('S7'!$B$6:$B$19,$A63,'S7'!$E$6:$E$19,"Ambos")+COUNTIFS('S8'!$B$6:$B$23,$A63,'S8'!$E$6:$E$23,"Víctor")+COUNTIFS('S8'!$B$6:$B$23,$A63,'S8'!$E$6:$E$23,"Ambos")+COUNTIFS('S9'!$B$6:$B$15,$A63,'S9'!$E$6:$E$15,"Víctor")+COUNTIFS('S9'!$B$6:$B$15,$A63,'S9'!$E$6:$E$15,"Ambos")+COUNTIFS('S10'!$B$6:$B$13,$A63,'S10'!$E$6:$E$13,"Víctor")+COUNTIFS('S10'!$B$6:$B$13,$A63,'S10'!$E$6:$E$13,"Ambos")+COUNTIFS('Holgura'!$B$6:$B$11,$A63,'Holgura'!$E$6:$E$11,"Víctor")+COUNTIFS('Holgura'!$B$6:$B$11,$A63,'Holgura'!$E$6:$E$11,"Ambos")+COUNTIFS('Entrega'!$B$6:$B$9,$A63,'Entrega'!$E$6:$E$9,"Víctor")+COUNTIFS('Entrega'!$B$6:$B$9,$A63,'Entrega'!$E$6:$E$9,"Ambos")+COUNTIFS('Defensa'!$B$6:$B$10,$A63,'Defensa'!$E$6:$E$10,"Víctor")+COUNTIFS('Defensa'!$B$6:$B$10,$A63,'Defensa'!$E$6:$E$10,"Ambos")</f>
         <v/>
       </c>
       <c r="G63" s="21">
-        <f>COUNTIFS('S1'!$B$6:$B$32,$A63,'S1'!$E$6:$E$32,"Diego")+COUNTIFS('S1'!$B$6:$B$32,$A63,'S1'!$E$6:$E$32,"Ambos")+COUNTIFS('S2'!$B$6:$B$23,$A63,'S2'!$E$6:$E$23,"Diego")+COUNTIFS('S2'!$B$6:$B$23,$A63,'S2'!$E$6:$E$23,"Ambos")+COUNTIFS('S3'!$B$6:$B$19,$A63,'S3'!$E$6:$E$19,"Diego")+COUNTIFS('S3'!$B$6:$B$19,$A63,'S3'!$E$6:$E$19,"Ambos")+COUNTIFS('S4'!$B$6:$B$20,$A63,'S4'!$E$6:$E$20,"Diego")+COUNTIFS('S4'!$B$6:$B$20,$A63,'S4'!$E$6:$E$20,"Ambos")+COUNTIFS('S5'!$B$6:$B$20,$A63,'S5'!$E$6:$E$20,"Diego")+COUNTIFS('S5'!$B$6:$B$20,$A63,'S5'!$E$6:$E$20,"Ambos")+COUNTIFS('S6'!$B$6:$B$17,$A63,'S6'!$E$6:$E$17,"Diego")+COUNTIFS('S6'!$B$6:$B$17,$A63,'S6'!$E$6:$E$17,"Ambos")+COUNTIFS('S7'!$B$6:$B$19,$A63,'S7'!$E$6:$E$19,"Diego")+COUNTIFS('S7'!$B$6:$B$19,$A63,'S7'!$E$6:$E$19,"Ambos")+COUNTIFS('S8'!$B$6:$B$23,$A63,'S8'!$E$6:$E$23,"Diego")+COUNTIFS('S8'!$B$6:$B$23,$A63,'S8'!$E$6:$E$23,"Ambos")+COUNTIFS('S9'!$B$6:$B$15,$A63,'S9'!$E$6:$E$15,"Diego")+COUNTIFS('S9'!$B$6:$B$15,$A63,'S9'!$E$6:$E$15,"Ambos")+COUNTIFS('S10'!$B$6:$B$13,$A63,'S10'!$E$6:$E$13,"Diego")+COUNTIFS('S10'!$B$6:$B$13,$A63,'S10'!$E$6:$E$13,"Ambos")+COUNTIFS('Holgura'!$B$6:$B$11,$A63,'Holgura'!$E$6:$E$11,"Diego")+COUNTIFS('Holgura'!$B$6:$B$11,$A63,'Holgura'!$E$6:$E$11,"Ambos")+COUNTIFS('Entrega'!$B$6:$B$9,$A63,'Entrega'!$E$6:$E$9,"Diego")+COUNTIFS('Entrega'!$B$6:$B$9,$A63,'Entrega'!$E$6:$E$9,"Ambos")+COUNTIFS('Defensa'!$B$6:$B$10,$A63,'Defensa'!$E$6:$E$10,"Diego")+COUNTIFS('Defensa'!$B$6:$B$10,$A63,'Defensa'!$E$6:$E$10,"Ambos")</f>
+        <f>COUNTIFS('S1'!$B$6:$B$32,$A63,'S1'!$E$6:$E$32,"Diego")+COUNTIFS('S1'!$B$6:$B$32,$A63,'S1'!$E$6:$E$32,"Ambos")+COUNTIFS('S2'!$B$6:$B$23,$A63,'S2'!$E$6:$E$23,"Diego")+COUNTIFS('S2'!$B$6:$B$23,$A63,'S2'!$E$6:$E$23,"Ambos")+COUNTIFS('S3'!$B$6:$B$24,$A63,'S3'!$E$6:$E$24,"Diego")+COUNTIFS('S3'!$B$6:$B$24,$A63,'S3'!$E$6:$E$24,"Ambos")+COUNTIFS('S4'!$B$6:$B$22,$A63,'S4'!$E$6:$E$22,"Diego")+COUNTIFS('S4'!$B$6:$B$22,$A63,'S4'!$E$6:$E$22,"Ambos")+COUNTIFS('S5'!$B$6:$B$20,$A63,'S5'!$E$6:$E$20,"Diego")+COUNTIFS('S5'!$B$6:$B$20,$A63,'S5'!$E$6:$E$20,"Ambos")+COUNTIFS('S6'!$B$6:$B$17,$A63,'S6'!$E$6:$E$17,"Diego")+COUNTIFS('S6'!$B$6:$B$17,$A63,'S6'!$E$6:$E$17,"Ambos")+COUNTIFS('S7'!$B$6:$B$19,$A63,'S7'!$E$6:$E$19,"Diego")+COUNTIFS('S7'!$B$6:$B$19,$A63,'S7'!$E$6:$E$19,"Ambos")+COUNTIFS('S8'!$B$6:$B$23,$A63,'S8'!$E$6:$E$23,"Diego")+COUNTIFS('S8'!$B$6:$B$23,$A63,'S8'!$E$6:$E$23,"Ambos")+COUNTIFS('S9'!$B$6:$B$15,$A63,'S9'!$E$6:$E$15,"Diego")+COUNTIFS('S9'!$B$6:$B$15,$A63,'S9'!$E$6:$E$15,"Ambos")+COUNTIFS('S10'!$B$6:$B$13,$A63,'S10'!$E$6:$E$13,"Diego")+COUNTIFS('S10'!$B$6:$B$13,$A63,'S10'!$E$6:$E$13,"Ambos")+COUNTIFS('Holgura'!$B$6:$B$11,$A63,'Holgura'!$E$6:$E$11,"Diego")+COUNTIFS('Holgura'!$B$6:$B$11,$A63,'Holgura'!$E$6:$E$11,"Ambos")+COUNTIFS('Entrega'!$B$6:$B$9,$A63,'Entrega'!$E$6:$E$9,"Diego")+COUNTIFS('Entrega'!$B$6:$B$9,$A63,'Entrega'!$E$6:$E$9,"Ambos")+COUNTIFS('Defensa'!$B$6:$B$10,$A63,'Defensa'!$E$6:$E$10,"Diego")+COUNTIFS('Defensa'!$B$6:$B$10,$A63,'Defensa'!$E$6:$E$10,"Ambos")</f>
         <v/>
       </c>
     </row>
@@ -10391,19 +10412,19 @@
         <v/>
       </c>
       <c r="D64" s="21">
-        <f>SUMIFS('S1'!$I$6:$I$32,'S1'!$B$6:$B$32,$A64,'S1'!$E$6:$E$32,"Víctor")+SUMIFS('S1'!$I$6:$I$32,'S1'!$B$6:$B$32,$A64,'S1'!$E$6:$E$32,"Ambos")+SUMIFS('S2'!$I$6:$I$23,'S2'!$B$6:$B$23,$A64,'S2'!$E$6:$E$23,"Víctor")+SUMIFS('S2'!$I$6:$I$23,'S2'!$B$6:$B$23,$A64,'S2'!$E$6:$E$23,"Ambos")+SUMIFS('S3'!$I$6:$I$19,'S3'!$B$6:$B$19,$A64,'S3'!$E$6:$E$19,"Víctor")+SUMIFS('S3'!$I$6:$I$19,'S3'!$B$6:$B$19,$A64,'S3'!$E$6:$E$19,"Ambos")+SUMIFS('S4'!$I$6:$I$20,'S4'!$B$6:$B$20,$A64,'S4'!$E$6:$E$20,"Víctor")+SUMIFS('S4'!$I$6:$I$20,'S4'!$B$6:$B$20,$A64,'S4'!$E$6:$E$20,"Ambos")+SUMIFS('S5'!$I$6:$I$20,'S5'!$B$6:$B$20,$A64,'S5'!$E$6:$E$20,"Víctor")+SUMIFS('S5'!$I$6:$I$20,'S5'!$B$6:$B$20,$A64,'S5'!$E$6:$E$20,"Ambos")+SUMIFS('S6'!$I$6:$I$17,'S6'!$B$6:$B$17,$A64,'S6'!$E$6:$E$17,"Víctor")+SUMIFS('S6'!$I$6:$I$17,'S6'!$B$6:$B$17,$A64,'S6'!$E$6:$E$17,"Ambos")+SUMIFS('S7'!$I$6:$I$19,'S7'!$B$6:$B$19,$A64,'S7'!$E$6:$E$19,"Víctor")+SUMIFS('S7'!$I$6:$I$19,'S7'!$B$6:$B$19,$A64,'S7'!$E$6:$E$19,"Ambos")+SUMIFS('S8'!$I$6:$I$23,'S8'!$B$6:$B$23,$A64,'S8'!$E$6:$E$23,"Víctor")+SUMIFS('S8'!$I$6:$I$23,'S8'!$B$6:$B$23,$A64,'S8'!$E$6:$E$23,"Ambos")+SUMIFS('S9'!$I$6:$I$15,'S9'!$B$6:$B$15,$A64,'S9'!$E$6:$E$15,"Víctor")+SUMIFS('S9'!$I$6:$I$15,'S9'!$B$6:$B$15,$A64,'S9'!$E$6:$E$15,"Ambos")+SUMIFS('S10'!$I$6:$I$13,'S10'!$B$6:$B$13,$A64,'S10'!$E$6:$E$13,"Víctor")+SUMIFS('S10'!$I$6:$I$13,'S10'!$B$6:$B$13,$A64,'S10'!$E$6:$E$13,"Ambos")+SUMIFS('Holgura'!$I$6:$I$11,'Holgura'!$B$6:$B$11,$A64,'Holgura'!$E$6:$E$11,"Víctor")+SUMIFS('Holgura'!$I$6:$I$11,'Holgura'!$B$6:$B$11,$A64,'Holgura'!$E$6:$E$11,"Ambos")+SUMIFS('Entrega'!$I$6:$I$9,'Entrega'!$B$6:$B$9,$A64,'Entrega'!$E$6:$E$9,"Víctor")+SUMIFS('Entrega'!$I$6:$I$9,'Entrega'!$B$6:$B$9,$A64,'Entrega'!$E$6:$E$9,"Ambos")+SUMIFS('Defensa'!$I$6:$I$10,'Defensa'!$B$6:$B$10,$A64,'Defensa'!$E$6:$E$10,"Víctor")+SUMIFS('Defensa'!$I$6:$I$10,'Defensa'!$B$6:$B$10,$A64,'Defensa'!$E$6:$E$10,"Ambos")</f>
+        <f>SUMIFS('S1'!$I$6:$I$32,'S1'!$B$6:$B$32,$A64,'S1'!$E$6:$E$32,"Víctor")+SUMIFS('S1'!$I$6:$I$32,'S1'!$B$6:$B$32,$A64,'S1'!$E$6:$E$32,"Ambos")+SUMIFS('S2'!$I$6:$I$23,'S2'!$B$6:$B$23,$A64,'S2'!$E$6:$E$23,"Víctor")+SUMIFS('S2'!$I$6:$I$23,'S2'!$B$6:$B$23,$A64,'S2'!$E$6:$E$23,"Ambos")+SUMIFS('S3'!$I$6:$I$24,'S3'!$B$6:$B$24,$A64,'S3'!$E$6:$E$24,"Víctor")+SUMIFS('S3'!$I$6:$I$24,'S3'!$B$6:$B$24,$A64,'S3'!$E$6:$E$24,"Ambos")+SUMIFS('S4'!$I$6:$I$22,'S4'!$B$6:$B$22,$A64,'S4'!$E$6:$E$22,"Víctor")+SUMIFS('S4'!$I$6:$I$22,'S4'!$B$6:$B$22,$A64,'S4'!$E$6:$E$22,"Ambos")+SUMIFS('S5'!$I$6:$I$20,'S5'!$B$6:$B$20,$A64,'S5'!$E$6:$E$20,"Víctor")+SUMIFS('S5'!$I$6:$I$20,'S5'!$B$6:$B$20,$A64,'S5'!$E$6:$E$20,"Ambos")+SUMIFS('S6'!$I$6:$I$17,'S6'!$B$6:$B$17,$A64,'S6'!$E$6:$E$17,"Víctor")+SUMIFS('S6'!$I$6:$I$17,'S6'!$B$6:$B$17,$A64,'S6'!$E$6:$E$17,"Ambos")+SUMIFS('S7'!$I$6:$I$19,'S7'!$B$6:$B$19,$A64,'S7'!$E$6:$E$19,"Víctor")+SUMIFS('S7'!$I$6:$I$19,'S7'!$B$6:$B$19,$A64,'S7'!$E$6:$E$19,"Ambos")+SUMIFS('S8'!$I$6:$I$23,'S8'!$B$6:$B$23,$A64,'S8'!$E$6:$E$23,"Víctor")+SUMIFS('S8'!$I$6:$I$23,'S8'!$B$6:$B$23,$A64,'S8'!$E$6:$E$23,"Ambos")+SUMIFS('S9'!$I$6:$I$15,'S9'!$B$6:$B$15,$A64,'S9'!$E$6:$E$15,"Víctor")+SUMIFS('S9'!$I$6:$I$15,'S9'!$B$6:$B$15,$A64,'S9'!$E$6:$E$15,"Ambos")+SUMIFS('S10'!$I$6:$I$13,'S10'!$B$6:$B$13,$A64,'S10'!$E$6:$E$13,"Víctor")+SUMIFS('S10'!$I$6:$I$13,'S10'!$B$6:$B$13,$A64,'S10'!$E$6:$E$13,"Ambos")+SUMIFS('Holgura'!$I$6:$I$11,'Holgura'!$B$6:$B$11,$A64,'Holgura'!$E$6:$E$11,"Víctor")+SUMIFS('Holgura'!$I$6:$I$11,'Holgura'!$B$6:$B$11,$A64,'Holgura'!$E$6:$E$11,"Ambos")+SUMIFS('Entrega'!$I$6:$I$9,'Entrega'!$B$6:$B$9,$A64,'Entrega'!$E$6:$E$9,"Víctor")+SUMIFS('Entrega'!$I$6:$I$9,'Entrega'!$B$6:$B$9,$A64,'Entrega'!$E$6:$E$9,"Ambos")+SUMIFS('Defensa'!$I$6:$I$10,'Defensa'!$B$6:$B$10,$A64,'Defensa'!$E$6:$E$10,"Víctor")+SUMIFS('Defensa'!$I$6:$I$10,'Defensa'!$B$6:$B$10,$A64,'Defensa'!$E$6:$E$10,"Ambos")</f>
         <v/>
       </c>
       <c r="E64" s="21">
-        <f>SUMIFS('S1'!$I$6:$I$32,'S1'!$B$6:$B$32,$A64,'S1'!$E$6:$E$32,"Diego")+SUMIFS('S1'!$I$6:$I$32,'S1'!$B$6:$B$32,$A64,'S1'!$E$6:$E$32,"Ambos")+SUMIFS('S2'!$I$6:$I$23,'S2'!$B$6:$B$23,$A64,'S2'!$E$6:$E$23,"Diego")+SUMIFS('S2'!$I$6:$I$23,'S2'!$B$6:$B$23,$A64,'S2'!$E$6:$E$23,"Ambos")+SUMIFS('S3'!$I$6:$I$19,'S3'!$B$6:$B$19,$A64,'S3'!$E$6:$E$19,"Diego")+SUMIFS('S3'!$I$6:$I$19,'S3'!$B$6:$B$19,$A64,'S3'!$E$6:$E$19,"Ambos")+SUMIFS('S4'!$I$6:$I$20,'S4'!$B$6:$B$20,$A64,'S4'!$E$6:$E$20,"Diego")+SUMIFS('S4'!$I$6:$I$20,'S4'!$B$6:$B$20,$A64,'S4'!$E$6:$E$20,"Ambos")+SUMIFS('S5'!$I$6:$I$20,'S5'!$B$6:$B$20,$A64,'S5'!$E$6:$E$20,"Diego")+SUMIFS('S5'!$I$6:$I$20,'S5'!$B$6:$B$20,$A64,'S5'!$E$6:$E$20,"Ambos")+SUMIFS('S6'!$I$6:$I$17,'S6'!$B$6:$B$17,$A64,'S6'!$E$6:$E$17,"Diego")+SUMIFS('S6'!$I$6:$I$17,'S6'!$B$6:$B$17,$A64,'S6'!$E$6:$E$17,"Ambos")+SUMIFS('S7'!$I$6:$I$19,'S7'!$B$6:$B$19,$A64,'S7'!$E$6:$E$19,"Diego")+SUMIFS('S7'!$I$6:$I$19,'S7'!$B$6:$B$19,$A64,'S7'!$E$6:$E$19,"Ambos")+SUMIFS('S8'!$I$6:$I$23,'S8'!$B$6:$B$23,$A64,'S8'!$E$6:$E$23,"Diego")+SUMIFS('S8'!$I$6:$I$23,'S8'!$B$6:$B$23,$A64,'S8'!$E$6:$E$23,"Ambos")+SUMIFS('S9'!$I$6:$I$15,'S9'!$B$6:$B$15,$A64,'S9'!$E$6:$E$15,"Diego")+SUMIFS('S9'!$I$6:$I$15,'S9'!$B$6:$B$15,$A64,'S9'!$E$6:$E$15,"Ambos")+SUMIFS('S10'!$I$6:$I$13,'S10'!$B$6:$B$13,$A64,'S10'!$E$6:$E$13,"Diego")+SUMIFS('S10'!$I$6:$I$13,'S10'!$B$6:$B$13,$A64,'S10'!$E$6:$E$13,"Ambos")+SUMIFS('Holgura'!$I$6:$I$11,'Holgura'!$B$6:$B$11,$A64,'Holgura'!$E$6:$E$11,"Diego")+SUMIFS('Holgura'!$I$6:$I$11,'Holgura'!$B$6:$B$11,$A64,'Holgura'!$E$6:$E$11,"Ambos")+SUMIFS('Entrega'!$I$6:$I$9,'Entrega'!$B$6:$B$9,$A64,'Entrega'!$E$6:$E$9,"Diego")+SUMIFS('Entrega'!$I$6:$I$9,'Entrega'!$B$6:$B$9,$A64,'Entrega'!$E$6:$E$9,"Ambos")+SUMIFS('Defensa'!$I$6:$I$10,'Defensa'!$B$6:$B$10,$A64,'Defensa'!$E$6:$E$10,"Diego")+SUMIFS('Defensa'!$I$6:$I$10,'Defensa'!$B$6:$B$10,$A64,'Defensa'!$E$6:$E$10,"Ambos")</f>
+        <f>SUMIFS('S1'!$I$6:$I$32,'S1'!$B$6:$B$32,$A64,'S1'!$E$6:$E$32,"Diego")+SUMIFS('S1'!$I$6:$I$32,'S1'!$B$6:$B$32,$A64,'S1'!$E$6:$E$32,"Ambos")+SUMIFS('S2'!$I$6:$I$23,'S2'!$B$6:$B$23,$A64,'S2'!$E$6:$E$23,"Diego")+SUMIFS('S2'!$I$6:$I$23,'S2'!$B$6:$B$23,$A64,'S2'!$E$6:$E$23,"Ambos")+SUMIFS('S3'!$I$6:$I$24,'S3'!$B$6:$B$24,$A64,'S3'!$E$6:$E$24,"Diego")+SUMIFS('S3'!$I$6:$I$24,'S3'!$B$6:$B$24,$A64,'S3'!$E$6:$E$24,"Ambos")+SUMIFS('S4'!$I$6:$I$22,'S4'!$B$6:$B$22,$A64,'S4'!$E$6:$E$22,"Diego")+SUMIFS('S4'!$I$6:$I$22,'S4'!$B$6:$B$22,$A64,'S4'!$E$6:$E$22,"Ambos")+SUMIFS('S5'!$I$6:$I$20,'S5'!$B$6:$B$20,$A64,'S5'!$E$6:$E$20,"Diego")+SUMIFS('S5'!$I$6:$I$20,'S5'!$B$6:$B$20,$A64,'S5'!$E$6:$E$20,"Ambos")+SUMIFS('S6'!$I$6:$I$17,'S6'!$B$6:$B$17,$A64,'S6'!$E$6:$E$17,"Diego")+SUMIFS('S6'!$I$6:$I$17,'S6'!$B$6:$B$17,$A64,'S6'!$E$6:$E$17,"Ambos")+SUMIFS('S7'!$I$6:$I$19,'S7'!$B$6:$B$19,$A64,'S7'!$E$6:$E$19,"Diego")+SUMIFS('S7'!$I$6:$I$19,'S7'!$B$6:$B$19,$A64,'S7'!$E$6:$E$19,"Ambos")+SUMIFS('S8'!$I$6:$I$23,'S8'!$B$6:$B$23,$A64,'S8'!$E$6:$E$23,"Diego")+SUMIFS('S8'!$I$6:$I$23,'S8'!$B$6:$B$23,$A64,'S8'!$E$6:$E$23,"Ambos")+SUMIFS('S9'!$I$6:$I$15,'S9'!$B$6:$B$15,$A64,'S9'!$E$6:$E$15,"Diego")+SUMIFS('S9'!$I$6:$I$15,'S9'!$B$6:$B$15,$A64,'S9'!$E$6:$E$15,"Ambos")+SUMIFS('S10'!$I$6:$I$13,'S10'!$B$6:$B$13,$A64,'S10'!$E$6:$E$13,"Diego")+SUMIFS('S10'!$I$6:$I$13,'S10'!$B$6:$B$13,$A64,'S10'!$E$6:$E$13,"Ambos")+SUMIFS('Holgura'!$I$6:$I$11,'Holgura'!$B$6:$B$11,$A64,'Holgura'!$E$6:$E$11,"Diego")+SUMIFS('Holgura'!$I$6:$I$11,'Holgura'!$B$6:$B$11,$A64,'Holgura'!$E$6:$E$11,"Ambos")+SUMIFS('Entrega'!$I$6:$I$9,'Entrega'!$B$6:$B$9,$A64,'Entrega'!$E$6:$E$9,"Diego")+SUMIFS('Entrega'!$I$6:$I$9,'Entrega'!$B$6:$B$9,$A64,'Entrega'!$E$6:$E$9,"Ambos")+SUMIFS('Defensa'!$I$6:$I$10,'Defensa'!$B$6:$B$10,$A64,'Defensa'!$E$6:$E$10,"Diego")+SUMIFS('Defensa'!$I$6:$I$10,'Defensa'!$B$6:$B$10,$A64,'Defensa'!$E$6:$E$10,"Ambos")</f>
         <v/>
       </c>
       <c r="F64" s="21">
-        <f>COUNTIFS('S1'!$B$6:$B$32,$A64,'S1'!$E$6:$E$32,"Víctor")+COUNTIFS('S1'!$B$6:$B$32,$A64,'S1'!$E$6:$E$32,"Ambos")+COUNTIFS('S2'!$B$6:$B$23,$A64,'S2'!$E$6:$E$23,"Víctor")+COUNTIFS('S2'!$B$6:$B$23,$A64,'S2'!$E$6:$E$23,"Ambos")+COUNTIFS('S3'!$B$6:$B$19,$A64,'S3'!$E$6:$E$19,"Víctor")+COUNTIFS('S3'!$B$6:$B$19,$A64,'S3'!$E$6:$E$19,"Ambos")+COUNTIFS('S4'!$B$6:$B$20,$A64,'S4'!$E$6:$E$20,"Víctor")+COUNTIFS('S4'!$B$6:$B$20,$A64,'S4'!$E$6:$E$20,"Ambos")+COUNTIFS('S5'!$B$6:$B$20,$A64,'S5'!$E$6:$E$20,"Víctor")+COUNTIFS('S5'!$B$6:$B$20,$A64,'S5'!$E$6:$E$20,"Ambos")+COUNTIFS('S6'!$B$6:$B$17,$A64,'S6'!$E$6:$E$17,"Víctor")+COUNTIFS('S6'!$B$6:$B$17,$A64,'S6'!$E$6:$E$17,"Ambos")+COUNTIFS('S7'!$B$6:$B$19,$A64,'S7'!$E$6:$E$19,"Víctor")+COUNTIFS('S7'!$B$6:$B$19,$A64,'S7'!$E$6:$E$19,"Ambos")+COUNTIFS('S8'!$B$6:$B$23,$A64,'S8'!$E$6:$E$23,"Víctor")+COUNTIFS('S8'!$B$6:$B$23,$A64,'S8'!$E$6:$E$23,"Ambos")+COUNTIFS('S9'!$B$6:$B$15,$A64,'S9'!$E$6:$E$15,"Víctor")+COUNTIFS('S9'!$B$6:$B$15,$A64,'S9'!$E$6:$E$15,"Ambos")+COUNTIFS('S10'!$B$6:$B$13,$A64,'S10'!$E$6:$E$13,"Víctor")+COUNTIFS('S10'!$B$6:$B$13,$A64,'S10'!$E$6:$E$13,"Ambos")+COUNTIFS('Holgura'!$B$6:$B$11,$A64,'Holgura'!$E$6:$E$11,"Víctor")+COUNTIFS('Holgura'!$B$6:$B$11,$A64,'Holgura'!$E$6:$E$11,"Ambos")+COUNTIFS('Entrega'!$B$6:$B$9,$A64,'Entrega'!$E$6:$E$9,"Víctor")+COUNTIFS('Entrega'!$B$6:$B$9,$A64,'Entrega'!$E$6:$E$9,"Ambos")+COUNTIFS('Defensa'!$B$6:$B$10,$A64,'Defensa'!$E$6:$E$10,"Víctor")+COUNTIFS('Defensa'!$B$6:$B$10,$A64,'Defensa'!$E$6:$E$10,"Ambos")</f>
+        <f>COUNTIFS('S1'!$B$6:$B$32,$A64,'S1'!$E$6:$E$32,"Víctor")+COUNTIFS('S1'!$B$6:$B$32,$A64,'S1'!$E$6:$E$32,"Ambos")+COUNTIFS('S2'!$B$6:$B$23,$A64,'S2'!$E$6:$E$23,"Víctor")+COUNTIFS('S2'!$B$6:$B$23,$A64,'S2'!$E$6:$E$23,"Ambos")+COUNTIFS('S3'!$B$6:$B$24,$A64,'S3'!$E$6:$E$24,"Víctor")+COUNTIFS('S3'!$B$6:$B$24,$A64,'S3'!$E$6:$E$24,"Ambos")+COUNTIFS('S4'!$B$6:$B$22,$A64,'S4'!$E$6:$E$22,"Víctor")+COUNTIFS('S4'!$B$6:$B$22,$A64,'S4'!$E$6:$E$22,"Ambos")+COUNTIFS('S5'!$B$6:$B$20,$A64,'S5'!$E$6:$E$20,"Víctor")+COUNTIFS('S5'!$B$6:$B$20,$A64,'S5'!$E$6:$E$20,"Ambos")+COUNTIFS('S6'!$B$6:$B$17,$A64,'S6'!$E$6:$E$17,"Víctor")+COUNTIFS('S6'!$B$6:$B$17,$A64,'S6'!$E$6:$E$17,"Ambos")+COUNTIFS('S7'!$B$6:$B$19,$A64,'S7'!$E$6:$E$19,"Víctor")+COUNTIFS('S7'!$B$6:$B$19,$A64,'S7'!$E$6:$E$19,"Ambos")+COUNTIFS('S8'!$B$6:$B$23,$A64,'S8'!$E$6:$E$23,"Víctor")+COUNTIFS('S8'!$B$6:$B$23,$A64,'S8'!$E$6:$E$23,"Ambos")+COUNTIFS('S9'!$B$6:$B$15,$A64,'S9'!$E$6:$E$15,"Víctor")+COUNTIFS('S9'!$B$6:$B$15,$A64,'S9'!$E$6:$E$15,"Ambos")+COUNTIFS('S10'!$B$6:$B$13,$A64,'S10'!$E$6:$E$13,"Víctor")+COUNTIFS('S10'!$B$6:$B$13,$A64,'S10'!$E$6:$E$13,"Ambos")+COUNTIFS('Holgura'!$B$6:$B$11,$A64,'Holgura'!$E$6:$E$11,"Víctor")+COUNTIFS('Holgura'!$B$6:$B$11,$A64,'Holgura'!$E$6:$E$11,"Ambos")+COUNTIFS('Entrega'!$B$6:$B$9,$A64,'Entrega'!$E$6:$E$9,"Víctor")+COUNTIFS('Entrega'!$B$6:$B$9,$A64,'Entrega'!$E$6:$E$9,"Ambos")+COUNTIFS('Defensa'!$B$6:$B$10,$A64,'Defensa'!$E$6:$E$10,"Víctor")+COUNTIFS('Defensa'!$B$6:$B$10,$A64,'Defensa'!$E$6:$E$10,"Ambos")</f>
         <v/>
       </c>
       <c r="G64" s="21">
-        <f>COUNTIFS('S1'!$B$6:$B$32,$A64,'S1'!$E$6:$E$32,"Diego")+COUNTIFS('S1'!$B$6:$B$32,$A64,'S1'!$E$6:$E$32,"Ambos")+COUNTIFS('S2'!$B$6:$B$23,$A64,'S2'!$E$6:$E$23,"Diego")+COUNTIFS('S2'!$B$6:$B$23,$A64,'S2'!$E$6:$E$23,"Ambos")+COUNTIFS('S3'!$B$6:$B$19,$A64,'S3'!$E$6:$E$19,"Diego")+COUNTIFS('S3'!$B$6:$B$19,$A64,'S3'!$E$6:$E$19,"Ambos")+COUNTIFS('S4'!$B$6:$B$20,$A64,'S4'!$E$6:$E$20,"Diego")+COUNTIFS('S4'!$B$6:$B$20,$A64,'S4'!$E$6:$E$20,"Ambos")+COUNTIFS('S5'!$B$6:$B$20,$A64,'S5'!$E$6:$E$20,"Diego")+COUNTIFS('S5'!$B$6:$B$20,$A64,'S5'!$E$6:$E$20,"Ambos")+COUNTIFS('S6'!$B$6:$B$17,$A64,'S6'!$E$6:$E$17,"Diego")+COUNTIFS('S6'!$B$6:$B$17,$A64,'S6'!$E$6:$E$17,"Ambos")+COUNTIFS('S7'!$B$6:$B$19,$A64,'S7'!$E$6:$E$19,"Diego")+COUNTIFS('S7'!$B$6:$B$19,$A64,'S7'!$E$6:$E$19,"Ambos")+COUNTIFS('S8'!$B$6:$B$23,$A64,'S8'!$E$6:$E$23,"Diego")+COUNTIFS('S8'!$B$6:$B$23,$A64,'S8'!$E$6:$E$23,"Ambos")+COUNTIFS('S9'!$B$6:$B$15,$A64,'S9'!$E$6:$E$15,"Diego")+COUNTIFS('S9'!$B$6:$B$15,$A64,'S9'!$E$6:$E$15,"Ambos")+COUNTIFS('S10'!$B$6:$B$13,$A64,'S10'!$E$6:$E$13,"Diego")+COUNTIFS('S10'!$B$6:$B$13,$A64,'S10'!$E$6:$E$13,"Ambos")+COUNTIFS('Holgura'!$B$6:$B$11,$A64,'Holgura'!$E$6:$E$11,"Diego")+COUNTIFS('Holgura'!$B$6:$B$11,$A64,'Holgura'!$E$6:$E$11,"Ambos")+COUNTIFS('Entrega'!$B$6:$B$9,$A64,'Entrega'!$E$6:$E$9,"Diego")+COUNTIFS('Entrega'!$B$6:$B$9,$A64,'Entrega'!$E$6:$E$9,"Ambos")+COUNTIFS('Defensa'!$B$6:$B$10,$A64,'Defensa'!$E$6:$E$10,"Diego")+COUNTIFS('Defensa'!$B$6:$B$10,$A64,'Defensa'!$E$6:$E$10,"Ambos")</f>
+        <f>COUNTIFS('S1'!$B$6:$B$32,$A64,'S1'!$E$6:$E$32,"Diego")+COUNTIFS('S1'!$B$6:$B$32,$A64,'S1'!$E$6:$E$32,"Ambos")+COUNTIFS('S2'!$B$6:$B$23,$A64,'S2'!$E$6:$E$23,"Diego")+COUNTIFS('S2'!$B$6:$B$23,$A64,'S2'!$E$6:$E$23,"Ambos")+COUNTIFS('S3'!$B$6:$B$24,$A64,'S3'!$E$6:$E$24,"Diego")+COUNTIFS('S3'!$B$6:$B$24,$A64,'S3'!$E$6:$E$24,"Ambos")+COUNTIFS('S4'!$B$6:$B$22,$A64,'S4'!$E$6:$E$22,"Diego")+COUNTIFS('S4'!$B$6:$B$22,$A64,'S4'!$E$6:$E$22,"Ambos")+COUNTIFS('S5'!$B$6:$B$20,$A64,'S5'!$E$6:$E$20,"Diego")+COUNTIFS('S5'!$B$6:$B$20,$A64,'S5'!$E$6:$E$20,"Ambos")+COUNTIFS('S6'!$B$6:$B$17,$A64,'S6'!$E$6:$E$17,"Diego")+COUNTIFS('S6'!$B$6:$B$17,$A64,'S6'!$E$6:$E$17,"Ambos")+COUNTIFS('S7'!$B$6:$B$19,$A64,'S7'!$E$6:$E$19,"Diego")+COUNTIFS('S7'!$B$6:$B$19,$A64,'S7'!$E$6:$E$19,"Ambos")+COUNTIFS('S8'!$B$6:$B$23,$A64,'S8'!$E$6:$E$23,"Diego")+COUNTIFS('S8'!$B$6:$B$23,$A64,'S8'!$E$6:$E$23,"Ambos")+COUNTIFS('S9'!$B$6:$B$15,$A64,'S9'!$E$6:$E$15,"Diego")+COUNTIFS('S9'!$B$6:$B$15,$A64,'S9'!$E$6:$E$15,"Ambos")+COUNTIFS('S10'!$B$6:$B$13,$A64,'S10'!$E$6:$E$13,"Diego")+COUNTIFS('S10'!$B$6:$B$13,$A64,'S10'!$E$6:$E$13,"Ambos")+COUNTIFS('Holgura'!$B$6:$B$11,$A64,'Holgura'!$E$6:$E$11,"Diego")+COUNTIFS('Holgura'!$B$6:$B$11,$A64,'Holgura'!$E$6:$E$11,"Ambos")+COUNTIFS('Entrega'!$B$6:$B$9,$A64,'Entrega'!$E$6:$E$9,"Diego")+COUNTIFS('Entrega'!$B$6:$B$9,$A64,'Entrega'!$E$6:$E$9,"Ambos")+COUNTIFS('Defensa'!$B$6:$B$10,$A64,'Defensa'!$E$6:$E$10,"Diego")+COUNTIFS('Defensa'!$B$6:$B$10,$A64,'Defensa'!$E$6:$E$10,"Ambos")</f>
         <v/>
       </c>
     </row>
@@ -10420,19 +10441,19 @@
         <v/>
       </c>
       <c r="D65" s="21">
-        <f>SUMIFS('S1'!$I$6:$I$32,'S1'!$B$6:$B$32,$A65,'S1'!$E$6:$E$32,"Víctor")+SUMIFS('S1'!$I$6:$I$32,'S1'!$B$6:$B$32,$A65,'S1'!$E$6:$E$32,"Ambos")+SUMIFS('S2'!$I$6:$I$23,'S2'!$B$6:$B$23,$A65,'S2'!$E$6:$E$23,"Víctor")+SUMIFS('S2'!$I$6:$I$23,'S2'!$B$6:$B$23,$A65,'S2'!$E$6:$E$23,"Ambos")+SUMIFS('S3'!$I$6:$I$19,'S3'!$B$6:$B$19,$A65,'S3'!$E$6:$E$19,"Víctor")+SUMIFS('S3'!$I$6:$I$19,'S3'!$B$6:$B$19,$A65,'S3'!$E$6:$E$19,"Ambos")+SUMIFS('S4'!$I$6:$I$20,'S4'!$B$6:$B$20,$A65,'S4'!$E$6:$E$20,"Víctor")+SUMIFS('S4'!$I$6:$I$20,'S4'!$B$6:$B$20,$A65,'S4'!$E$6:$E$20,"Ambos")+SUMIFS('S5'!$I$6:$I$20,'S5'!$B$6:$B$20,$A65,'S5'!$E$6:$E$20,"Víctor")+SUMIFS('S5'!$I$6:$I$20,'S5'!$B$6:$B$20,$A65,'S5'!$E$6:$E$20,"Ambos")+SUMIFS('S6'!$I$6:$I$17,'S6'!$B$6:$B$17,$A65,'S6'!$E$6:$E$17,"Víctor")+SUMIFS('S6'!$I$6:$I$17,'S6'!$B$6:$B$17,$A65,'S6'!$E$6:$E$17,"Ambos")+SUMIFS('S7'!$I$6:$I$19,'S7'!$B$6:$B$19,$A65,'S7'!$E$6:$E$19,"Víctor")+SUMIFS('S7'!$I$6:$I$19,'S7'!$B$6:$B$19,$A65,'S7'!$E$6:$E$19,"Ambos")+SUMIFS('S8'!$I$6:$I$23,'S8'!$B$6:$B$23,$A65,'S8'!$E$6:$E$23,"Víctor")+SUMIFS('S8'!$I$6:$I$23,'S8'!$B$6:$B$23,$A65,'S8'!$E$6:$E$23,"Ambos")+SUMIFS('S9'!$I$6:$I$15,'S9'!$B$6:$B$15,$A65,'S9'!$E$6:$E$15,"Víctor")+SUMIFS('S9'!$I$6:$I$15,'S9'!$B$6:$B$15,$A65,'S9'!$E$6:$E$15,"Ambos")+SUMIFS('S10'!$I$6:$I$13,'S10'!$B$6:$B$13,$A65,'S10'!$E$6:$E$13,"Víctor")+SUMIFS('S10'!$I$6:$I$13,'S10'!$B$6:$B$13,$A65,'S10'!$E$6:$E$13,"Ambos")+SUMIFS('Holgura'!$I$6:$I$11,'Holgura'!$B$6:$B$11,$A65,'Holgura'!$E$6:$E$11,"Víctor")+SUMIFS('Holgura'!$I$6:$I$11,'Holgura'!$B$6:$B$11,$A65,'Holgura'!$E$6:$E$11,"Ambos")+SUMIFS('Entrega'!$I$6:$I$9,'Entrega'!$B$6:$B$9,$A65,'Entrega'!$E$6:$E$9,"Víctor")+SUMIFS('Entrega'!$I$6:$I$9,'Entrega'!$B$6:$B$9,$A65,'Entrega'!$E$6:$E$9,"Ambos")+SUMIFS('Defensa'!$I$6:$I$10,'Defensa'!$B$6:$B$10,$A65,'Defensa'!$E$6:$E$10,"Víctor")+SUMIFS('Defensa'!$I$6:$I$10,'Defensa'!$B$6:$B$10,$A65,'Defensa'!$E$6:$E$10,"Ambos")</f>
+        <f>SUMIFS('S1'!$I$6:$I$32,'S1'!$B$6:$B$32,$A65,'S1'!$E$6:$E$32,"Víctor")+SUMIFS('S1'!$I$6:$I$32,'S1'!$B$6:$B$32,$A65,'S1'!$E$6:$E$32,"Ambos")+SUMIFS('S2'!$I$6:$I$23,'S2'!$B$6:$B$23,$A65,'S2'!$E$6:$E$23,"Víctor")+SUMIFS('S2'!$I$6:$I$23,'S2'!$B$6:$B$23,$A65,'S2'!$E$6:$E$23,"Ambos")+SUMIFS('S3'!$I$6:$I$24,'S3'!$B$6:$B$24,$A65,'S3'!$E$6:$E$24,"Víctor")+SUMIFS('S3'!$I$6:$I$24,'S3'!$B$6:$B$24,$A65,'S3'!$E$6:$E$24,"Ambos")+SUMIFS('S4'!$I$6:$I$22,'S4'!$B$6:$B$22,$A65,'S4'!$E$6:$E$22,"Víctor")+SUMIFS('S4'!$I$6:$I$22,'S4'!$B$6:$B$22,$A65,'S4'!$E$6:$E$22,"Ambos")+SUMIFS('S5'!$I$6:$I$20,'S5'!$B$6:$B$20,$A65,'S5'!$E$6:$E$20,"Víctor")+SUMIFS('S5'!$I$6:$I$20,'S5'!$B$6:$B$20,$A65,'S5'!$E$6:$E$20,"Ambos")+SUMIFS('S6'!$I$6:$I$17,'S6'!$B$6:$B$17,$A65,'S6'!$E$6:$E$17,"Víctor")+SUMIFS('S6'!$I$6:$I$17,'S6'!$B$6:$B$17,$A65,'S6'!$E$6:$E$17,"Ambos")+SUMIFS('S7'!$I$6:$I$19,'S7'!$B$6:$B$19,$A65,'S7'!$E$6:$E$19,"Víctor")+SUMIFS('S7'!$I$6:$I$19,'S7'!$B$6:$B$19,$A65,'S7'!$E$6:$E$19,"Ambos")+SUMIFS('S8'!$I$6:$I$23,'S8'!$B$6:$B$23,$A65,'S8'!$E$6:$E$23,"Víctor")+SUMIFS('S8'!$I$6:$I$23,'S8'!$B$6:$B$23,$A65,'S8'!$E$6:$E$23,"Ambos")+SUMIFS('S9'!$I$6:$I$15,'S9'!$B$6:$B$15,$A65,'S9'!$E$6:$E$15,"Víctor")+SUMIFS('S9'!$I$6:$I$15,'S9'!$B$6:$B$15,$A65,'S9'!$E$6:$E$15,"Ambos")+SUMIFS('S10'!$I$6:$I$13,'S10'!$B$6:$B$13,$A65,'S10'!$E$6:$E$13,"Víctor")+SUMIFS('S10'!$I$6:$I$13,'S10'!$B$6:$B$13,$A65,'S10'!$E$6:$E$13,"Ambos")+SUMIFS('Holgura'!$I$6:$I$11,'Holgura'!$B$6:$B$11,$A65,'Holgura'!$E$6:$E$11,"Víctor")+SUMIFS('Holgura'!$I$6:$I$11,'Holgura'!$B$6:$B$11,$A65,'Holgura'!$E$6:$E$11,"Ambos")+SUMIFS('Entrega'!$I$6:$I$9,'Entrega'!$B$6:$B$9,$A65,'Entrega'!$E$6:$E$9,"Víctor")+SUMIFS('Entrega'!$I$6:$I$9,'Entrega'!$B$6:$B$9,$A65,'Entrega'!$E$6:$E$9,"Ambos")+SUMIFS('Defensa'!$I$6:$I$10,'Defensa'!$B$6:$B$10,$A65,'Defensa'!$E$6:$E$10,"Víctor")+SUMIFS('Defensa'!$I$6:$I$10,'Defensa'!$B$6:$B$10,$A65,'Defensa'!$E$6:$E$10,"Ambos")</f>
         <v/>
       </c>
       <c r="E65" s="21">
-        <f>SUMIFS('S1'!$I$6:$I$32,'S1'!$B$6:$B$32,$A65,'S1'!$E$6:$E$32,"Diego")+SUMIFS('S1'!$I$6:$I$32,'S1'!$B$6:$B$32,$A65,'S1'!$E$6:$E$32,"Ambos")+SUMIFS('S2'!$I$6:$I$23,'S2'!$B$6:$B$23,$A65,'S2'!$E$6:$E$23,"Diego")+SUMIFS('S2'!$I$6:$I$23,'S2'!$B$6:$B$23,$A65,'S2'!$E$6:$E$23,"Ambos")+SUMIFS('S3'!$I$6:$I$19,'S3'!$B$6:$B$19,$A65,'S3'!$E$6:$E$19,"Diego")+SUMIFS('S3'!$I$6:$I$19,'S3'!$B$6:$B$19,$A65,'S3'!$E$6:$E$19,"Ambos")+SUMIFS('S4'!$I$6:$I$20,'S4'!$B$6:$B$20,$A65,'S4'!$E$6:$E$20,"Diego")+SUMIFS('S4'!$I$6:$I$20,'S4'!$B$6:$B$20,$A65,'S4'!$E$6:$E$20,"Ambos")+SUMIFS('S5'!$I$6:$I$20,'S5'!$B$6:$B$20,$A65,'S5'!$E$6:$E$20,"Diego")+SUMIFS('S5'!$I$6:$I$20,'S5'!$B$6:$B$20,$A65,'S5'!$E$6:$E$20,"Ambos")+SUMIFS('S6'!$I$6:$I$17,'S6'!$B$6:$B$17,$A65,'S6'!$E$6:$E$17,"Diego")+SUMIFS('S6'!$I$6:$I$17,'S6'!$B$6:$B$17,$A65,'S6'!$E$6:$E$17,"Ambos")+SUMIFS('S7'!$I$6:$I$19,'S7'!$B$6:$B$19,$A65,'S7'!$E$6:$E$19,"Diego")+SUMIFS('S7'!$I$6:$I$19,'S7'!$B$6:$B$19,$A65,'S7'!$E$6:$E$19,"Ambos")+SUMIFS('S8'!$I$6:$I$23,'S8'!$B$6:$B$23,$A65,'S8'!$E$6:$E$23,"Diego")+SUMIFS('S8'!$I$6:$I$23,'S8'!$B$6:$B$23,$A65,'S8'!$E$6:$E$23,"Ambos")+SUMIFS('S9'!$I$6:$I$15,'S9'!$B$6:$B$15,$A65,'S9'!$E$6:$E$15,"Diego")+SUMIFS('S9'!$I$6:$I$15,'S9'!$B$6:$B$15,$A65,'S9'!$E$6:$E$15,"Ambos")+SUMIFS('S10'!$I$6:$I$13,'S10'!$B$6:$B$13,$A65,'S10'!$E$6:$E$13,"Diego")+SUMIFS('S10'!$I$6:$I$13,'S10'!$B$6:$B$13,$A65,'S10'!$E$6:$E$13,"Ambos")+SUMIFS('Holgura'!$I$6:$I$11,'Holgura'!$B$6:$B$11,$A65,'Holgura'!$E$6:$E$11,"Diego")+SUMIFS('Holgura'!$I$6:$I$11,'Holgura'!$B$6:$B$11,$A65,'Holgura'!$E$6:$E$11,"Ambos")+SUMIFS('Entrega'!$I$6:$I$9,'Entrega'!$B$6:$B$9,$A65,'Entrega'!$E$6:$E$9,"Diego")+SUMIFS('Entrega'!$I$6:$I$9,'Entrega'!$B$6:$B$9,$A65,'Entrega'!$E$6:$E$9,"Ambos")+SUMIFS('Defensa'!$I$6:$I$10,'Defensa'!$B$6:$B$10,$A65,'Defensa'!$E$6:$E$10,"Diego")+SUMIFS('Defensa'!$I$6:$I$10,'Defensa'!$B$6:$B$10,$A65,'Defensa'!$E$6:$E$10,"Ambos")</f>
+        <f>SUMIFS('S1'!$I$6:$I$32,'S1'!$B$6:$B$32,$A65,'S1'!$E$6:$E$32,"Diego")+SUMIFS('S1'!$I$6:$I$32,'S1'!$B$6:$B$32,$A65,'S1'!$E$6:$E$32,"Ambos")+SUMIFS('S2'!$I$6:$I$23,'S2'!$B$6:$B$23,$A65,'S2'!$E$6:$E$23,"Diego")+SUMIFS('S2'!$I$6:$I$23,'S2'!$B$6:$B$23,$A65,'S2'!$E$6:$E$23,"Ambos")+SUMIFS('S3'!$I$6:$I$24,'S3'!$B$6:$B$24,$A65,'S3'!$E$6:$E$24,"Diego")+SUMIFS('S3'!$I$6:$I$24,'S3'!$B$6:$B$24,$A65,'S3'!$E$6:$E$24,"Ambos")+SUMIFS('S4'!$I$6:$I$22,'S4'!$B$6:$B$22,$A65,'S4'!$E$6:$E$22,"Diego")+SUMIFS('S4'!$I$6:$I$22,'S4'!$B$6:$B$22,$A65,'S4'!$E$6:$E$22,"Ambos")+SUMIFS('S5'!$I$6:$I$20,'S5'!$B$6:$B$20,$A65,'S5'!$E$6:$E$20,"Diego")+SUMIFS('S5'!$I$6:$I$20,'S5'!$B$6:$B$20,$A65,'S5'!$E$6:$E$20,"Ambos")+SUMIFS('S6'!$I$6:$I$17,'S6'!$B$6:$B$17,$A65,'S6'!$E$6:$E$17,"Diego")+SUMIFS('S6'!$I$6:$I$17,'S6'!$B$6:$B$17,$A65,'S6'!$E$6:$E$17,"Ambos")+SUMIFS('S7'!$I$6:$I$19,'S7'!$B$6:$B$19,$A65,'S7'!$E$6:$E$19,"Diego")+SUMIFS('S7'!$I$6:$I$19,'S7'!$B$6:$B$19,$A65,'S7'!$E$6:$E$19,"Ambos")+SUMIFS('S8'!$I$6:$I$23,'S8'!$B$6:$B$23,$A65,'S8'!$E$6:$E$23,"Diego")+SUMIFS('S8'!$I$6:$I$23,'S8'!$B$6:$B$23,$A65,'S8'!$E$6:$E$23,"Ambos")+SUMIFS('S9'!$I$6:$I$15,'S9'!$B$6:$B$15,$A65,'S9'!$E$6:$E$15,"Diego")+SUMIFS('S9'!$I$6:$I$15,'S9'!$B$6:$B$15,$A65,'S9'!$E$6:$E$15,"Ambos")+SUMIFS('S10'!$I$6:$I$13,'S10'!$B$6:$B$13,$A65,'S10'!$E$6:$E$13,"Diego")+SUMIFS('S10'!$I$6:$I$13,'S10'!$B$6:$B$13,$A65,'S10'!$E$6:$E$13,"Ambos")+SUMIFS('Holgura'!$I$6:$I$11,'Holgura'!$B$6:$B$11,$A65,'Holgura'!$E$6:$E$11,"Diego")+SUMIFS('Holgura'!$I$6:$I$11,'Holgura'!$B$6:$B$11,$A65,'Holgura'!$E$6:$E$11,"Ambos")+SUMIFS('Entrega'!$I$6:$I$9,'Entrega'!$B$6:$B$9,$A65,'Entrega'!$E$6:$E$9,"Diego")+SUMIFS('Entrega'!$I$6:$I$9,'Entrega'!$B$6:$B$9,$A65,'Entrega'!$E$6:$E$9,"Ambos")+SUMIFS('Defensa'!$I$6:$I$10,'Defensa'!$B$6:$B$10,$A65,'Defensa'!$E$6:$E$10,"Diego")+SUMIFS('Defensa'!$I$6:$I$10,'Defensa'!$B$6:$B$10,$A65,'Defensa'!$E$6:$E$10,"Ambos")</f>
         <v/>
       </c>
       <c r="F65" s="21">
-        <f>COUNTIFS('S1'!$B$6:$B$32,$A65,'S1'!$E$6:$E$32,"Víctor")+COUNTIFS('S1'!$B$6:$B$32,$A65,'S1'!$E$6:$E$32,"Ambos")+COUNTIFS('S2'!$B$6:$B$23,$A65,'S2'!$E$6:$E$23,"Víctor")+COUNTIFS('S2'!$B$6:$B$23,$A65,'S2'!$E$6:$E$23,"Ambos")+COUNTIFS('S3'!$B$6:$B$19,$A65,'S3'!$E$6:$E$19,"Víctor")+COUNTIFS('S3'!$B$6:$B$19,$A65,'S3'!$E$6:$E$19,"Ambos")+COUNTIFS('S4'!$B$6:$B$20,$A65,'S4'!$E$6:$E$20,"Víctor")+COUNTIFS('S4'!$B$6:$B$20,$A65,'S4'!$E$6:$E$20,"Ambos")+COUNTIFS('S5'!$B$6:$B$20,$A65,'S5'!$E$6:$E$20,"Víctor")+COUNTIFS('S5'!$B$6:$B$20,$A65,'S5'!$E$6:$E$20,"Ambos")+COUNTIFS('S6'!$B$6:$B$17,$A65,'S6'!$E$6:$E$17,"Víctor")+COUNTIFS('S6'!$B$6:$B$17,$A65,'S6'!$E$6:$E$17,"Ambos")+COUNTIFS('S7'!$B$6:$B$19,$A65,'S7'!$E$6:$E$19,"Víctor")+COUNTIFS('S7'!$B$6:$B$19,$A65,'S7'!$E$6:$E$19,"Ambos")+COUNTIFS('S8'!$B$6:$B$23,$A65,'S8'!$E$6:$E$23,"Víctor")+COUNTIFS('S8'!$B$6:$B$23,$A65,'S8'!$E$6:$E$23,"Ambos")+COUNTIFS('S9'!$B$6:$B$15,$A65,'S9'!$E$6:$E$15,"Víctor")+COUNTIFS('S9'!$B$6:$B$15,$A65,'S9'!$E$6:$E$15,"Ambos")+COUNTIFS('S10'!$B$6:$B$13,$A65,'S10'!$E$6:$E$13,"Víctor")+COUNTIFS('S10'!$B$6:$B$13,$A65,'S10'!$E$6:$E$13,"Ambos")+COUNTIFS('Holgura'!$B$6:$B$11,$A65,'Holgura'!$E$6:$E$11,"Víctor")+COUNTIFS('Holgura'!$B$6:$B$11,$A65,'Holgura'!$E$6:$E$11,"Ambos")+COUNTIFS('Entrega'!$B$6:$B$9,$A65,'Entrega'!$E$6:$E$9,"Víctor")+COUNTIFS('Entrega'!$B$6:$B$9,$A65,'Entrega'!$E$6:$E$9,"Ambos")+COUNTIFS('Defensa'!$B$6:$B$10,$A65,'Defensa'!$E$6:$E$10,"Víctor")+COUNTIFS('Defensa'!$B$6:$B$10,$A65,'Defensa'!$E$6:$E$10,"Ambos")</f>
+        <f>COUNTIFS('S1'!$B$6:$B$32,$A65,'S1'!$E$6:$E$32,"Víctor")+COUNTIFS('S1'!$B$6:$B$32,$A65,'S1'!$E$6:$E$32,"Ambos")+COUNTIFS('S2'!$B$6:$B$23,$A65,'S2'!$E$6:$E$23,"Víctor")+COUNTIFS('S2'!$B$6:$B$23,$A65,'S2'!$E$6:$E$23,"Ambos")+COUNTIFS('S3'!$B$6:$B$24,$A65,'S3'!$E$6:$E$24,"Víctor")+COUNTIFS('S3'!$B$6:$B$24,$A65,'S3'!$E$6:$E$24,"Ambos")+COUNTIFS('S4'!$B$6:$B$22,$A65,'S4'!$E$6:$E$22,"Víctor")+COUNTIFS('S4'!$B$6:$B$22,$A65,'S4'!$E$6:$E$22,"Ambos")+COUNTIFS('S5'!$B$6:$B$20,$A65,'S5'!$E$6:$E$20,"Víctor")+COUNTIFS('S5'!$B$6:$B$20,$A65,'S5'!$E$6:$E$20,"Ambos")+COUNTIFS('S6'!$B$6:$B$17,$A65,'S6'!$E$6:$E$17,"Víctor")+COUNTIFS('S6'!$B$6:$B$17,$A65,'S6'!$E$6:$E$17,"Ambos")+COUNTIFS('S7'!$B$6:$B$19,$A65,'S7'!$E$6:$E$19,"Víctor")+COUNTIFS('S7'!$B$6:$B$19,$A65,'S7'!$E$6:$E$19,"Ambos")+COUNTIFS('S8'!$B$6:$B$23,$A65,'S8'!$E$6:$E$23,"Víctor")+COUNTIFS('S8'!$B$6:$B$23,$A65,'S8'!$E$6:$E$23,"Ambos")+COUNTIFS('S9'!$B$6:$B$15,$A65,'S9'!$E$6:$E$15,"Víctor")+COUNTIFS('S9'!$B$6:$B$15,$A65,'S9'!$E$6:$E$15,"Ambos")+COUNTIFS('S10'!$B$6:$B$13,$A65,'S10'!$E$6:$E$13,"Víctor")+COUNTIFS('S10'!$B$6:$B$13,$A65,'S10'!$E$6:$E$13,"Ambos")+COUNTIFS('Holgura'!$B$6:$B$11,$A65,'Holgura'!$E$6:$E$11,"Víctor")+COUNTIFS('Holgura'!$B$6:$B$11,$A65,'Holgura'!$E$6:$E$11,"Ambos")+COUNTIFS('Entrega'!$B$6:$B$9,$A65,'Entrega'!$E$6:$E$9,"Víctor")+COUNTIFS('Entrega'!$B$6:$B$9,$A65,'Entrega'!$E$6:$E$9,"Ambos")+COUNTIFS('Defensa'!$B$6:$B$10,$A65,'Defensa'!$E$6:$E$10,"Víctor")+COUNTIFS('Defensa'!$B$6:$B$10,$A65,'Defensa'!$E$6:$E$10,"Ambos")</f>
         <v/>
       </c>
       <c r="G65" s="21">
-        <f>COUNTIFS('S1'!$B$6:$B$32,$A65,'S1'!$E$6:$E$32,"Diego")+COUNTIFS('S1'!$B$6:$B$32,$A65,'S1'!$E$6:$E$32,"Ambos")+COUNTIFS('S2'!$B$6:$B$23,$A65,'S2'!$E$6:$E$23,"Diego")+COUNTIFS('S2'!$B$6:$B$23,$A65,'S2'!$E$6:$E$23,"Ambos")+COUNTIFS('S3'!$B$6:$B$19,$A65,'S3'!$E$6:$E$19,"Diego")+COUNTIFS('S3'!$B$6:$B$19,$A65,'S3'!$E$6:$E$19,"Ambos")+COUNTIFS('S4'!$B$6:$B$20,$A65,'S4'!$E$6:$E$20,"Diego")+COUNTIFS('S4'!$B$6:$B$20,$A65,'S4'!$E$6:$E$20,"Ambos")+COUNTIFS('S5'!$B$6:$B$20,$A65,'S5'!$E$6:$E$20,"Diego")+COUNTIFS('S5'!$B$6:$B$20,$A65,'S5'!$E$6:$E$20,"Ambos")+COUNTIFS('S6'!$B$6:$B$17,$A65,'S6'!$E$6:$E$17,"Diego")+COUNTIFS('S6'!$B$6:$B$17,$A65,'S6'!$E$6:$E$17,"Ambos")+COUNTIFS('S7'!$B$6:$B$19,$A65,'S7'!$E$6:$E$19,"Diego")+COUNTIFS('S7'!$B$6:$B$19,$A65,'S7'!$E$6:$E$19,"Ambos")+COUNTIFS('S8'!$B$6:$B$23,$A65,'S8'!$E$6:$E$23,"Diego")+COUNTIFS('S8'!$B$6:$B$23,$A65,'S8'!$E$6:$E$23,"Ambos")+COUNTIFS('S9'!$B$6:$B$15,$A65,'S9'!$E$6:$E$15,"Diego")+COUNTIFS('S9'!$B$6:$B$15,$A65,'S9'!$E$6:$E$15,"Ambos")+COUNTIFS('S10'!$B$6:$B$13,$A65,'S10'!$E$6:$E$13,"Diego")+COUNTIFS('S10'!$B$6:$B$13,$A65,'S10'!$E$6:$E$13,"Ambos")+COUNTIFS('Holgura'!$B$6:$B$11,$A65,'Holgura'!$E$6:$E$11,"Diego")+COUNTIFS('Holgura'!$B$6:$B$11,$A65,'Holgura'!$E$6:$E$11,"Ambos")+COUNTIFS('Entrega'!$B$6:$B$9,$A65,'Entrega'!$E$6:$E$9,"Diego")+COUNTIFS('Entrega'!$B$6:$B$9,$A65,'Entrega'!$E$6:$E$9,"Ambos")+COUNTIFS('Defensa'!$B$6:$B$10,$A65,'Defensa'!$E$6:$E$10,"Diego")+COUNTIFS('Defensa'!$B$6:$B$10,$A65,'Defensa'!$E$6:$E$10,"Ambos")</f>
+        <f>COUNTIFS('S1'!$B$6:$B$32,$A65,'S1'!$E$6:$E$32,"Diego")+COUNTIFS('S1'!$B$6:$B$32,$A65,'S1'!$E$6:$E$32,"Ambos")+COUNTIFS('S2'!$B$6:$B$23,$A65,'S2'!$E$6:$E$23,"Diego")+COUNTIFS('S2'!$B$6:$B$23,$A65,'S2'!$E$6:$E$23,"Ambos")+COUNTIFS('S3'!$B$6:$B$24,$A65,'S3'!$E$6:$E$24,"Diego")+COUNTIFS('S3'!$B$6:$B$24,$A65,'S3'!$E$6:$E$24,"Ambos")+COUNTIFS('S4'!$B$6:$B$22,$A65,'S4'!$E$6:$E$22,"Diego")+COUNTIFS('S4'!$B$6:$B$22,$A65,'S4'!$E$6:$E$22,"Ambos")+COUNTIFS('S5'!$B$6:$B$20,$A65,'S5'!$E$6:$E$20,"Diego")+COUNTIFS('S5'!$B$6:$B$20,$A65,'S5'!$E$6:$E$20,"Ambos")+COUNTIFS('S6'!$B$6:$B$17,$A65,'S6'!$E$6:$E$17,"Diego")+COUNTIFS('S6'!$B$6:$B$17,$A65,'S6'!$E$6:$E$17,"Ambos")+COUNTIFS('S7'!$B$6:$B$19,$A65,'S7'!$E$6:$E$19,"Diego")+COUNTIFS('S7'!$B$6:$B$19,$A65,'S7'!$E$6:$E$19,"Ambos")+COUNTIFS('S8'!$B$6:$B$23,$A65,'S8'!$E$6:$E$23,"Diego")+COUNTIFS('S8'!$B$6:$B$23,$A65,'S8'!$E$6:$E$23,"Ambos")+COUNTIFS('S9'!$B$6:$B$15,$A65,'S9'!$E$6:$E$15,"Diego")+COUNTIFS('S9'!$B$6:$B$15,$A65,'S9'!$E$6:$E$15,"Ambos")+COUNTIFS('S10'!$B$6:$B$13,$A65,'S10'!$E$6:$E$13,"Diego")+COUNTIFS('S10'!$B$6:$B$13,$A65,'S10'!$E$6:$E$13,"Ambos")+COUNTIFS('Holgura'!$B$6:$B$11,$A65,'Holgura'!$E$6:$E$11,"Diego")+COUNTIFS('Holgura'!$B$6:$B$11,$A65,'Holgura'!$E$6:$E$11,"Ambos")+COUNTIFS('Entrega'!$B$6:$B$9,$A65,'Entrega'!$E$6:$E$9,"Diego")+COUNTIFS('Entrega'!$B$6:$B$9,$A65,'Entrega'!$E$6:$E$9,"Ambos")+COUNTIFS('Defensa'!$B$6:$B$10,$A65,'Defensa'!$E$6:$E$10,"Diego")+COUNTIFS('Defensa'!$B$6:$B$10,$A65,'Defensa'!$E$6:$E$10,"Ambos")</f>
         <v/>
       </c>
     </row>
@@ -10449,19 +10470,19 @@
         <v/>
       </c>
       <c r="D66" s="21">
-        <f>SUMIFS('S1'!$I$6:$I$32,'S1'!$B$6:$B$32,$A66,'S1'!$E$6:$E$32,"Víctor")+SUMIFS('S1'!$I$6:$I$32,'S1'!$B$6:$B$32,$A66,'S1'!$E$6:$E$32,"Ambos")+SUMIFS('S2'!$I$6:$I$23,'S2'!$B$6:$B$23,$A66,'S2'!$E$6:$E$23,"Víctor")+SUMIFS('S2'!$I$6:$I$23,'S2'!$B$6:$B$23,$A66,'S2'!$E$6:$E$23,"Ambos")+SUMIFS('S3'!$I$6:$I$19,'S3'!$B$6:$B$19,$A66,'S3'!$E$6:$E$19,"Víctor")+SUMIFS('S3'!$I$6:$I$19,'S3'!$B$6:$B$19,$A66,'S3'!$E$6:$E$19,"Ambos")+SUMIFS('S4'!$I$6:$I$20,'S4'!$B$6:$B$20,$A66,'S4'!$E$6:$E$20,"Víctor")+SUMIFS('S4'!$I$6:$I$20,'S4'!$B$6:$B$20,$A66,'S4'!$E$6:$E$20,"Ambos")+SUMIFS('S5'!$I$6:$I$20,'S5'!$B$6:$B$20,$A66,'S5'!$E$6:$E$20,"Víctor")+SUMIFS('S5'!$I$6:$I$20,'S5'!$B$6:$B$20,$A66,'S5'!$E$6:$E$20,"Ambos")+SUMIFS('S6'!$I$6:$I$17,'S6'!$B$6:$B$17,$A66,'S6'!$E$6:$E$17,"Víctor")+SUMIFS('S6'!$I$6:$I$17,'S6'!$B$6:$B$17,$A66,'S6'!$E$6:$E$17,"Ambos")+SUMIFS('S7'!$I$6:$I$19,'S7'!$B$6:$B$19,$A66,'S7'!$E$6:$E$19,"Víctor")+SUMIFS('S7'!$I$6:$I$19,'S7'!$B$6:$B$19,$A66,'S7'!$E$6:$E$19,"Ambos")+SUMIFS('S8'!$I$6:$I$23,'S8'!$B$6:$B$23,$A66,'S8'!$E$6:$E$23,"Víctor")+SUMIFS('S8'!$I$6:$I$23,'S8'!$B$6:$B$23,$A66,'S8'!$E$6:$E$23,"Ambos")+SUMIFS('S9'!$I$6:$I$15,'S9'!$B$6:$B$15,$A66,'S9'!$E$6:$E$15,"Víctor")+SUMIFS('S9'!$I$6:$I$15,'S9'!$B$6:$B$15,$A66,'S9'!$E$6:$E$15,"Ambos")+SUMIFS('S10'!$I$6:$I$13,'S10'!$B$6:$B$13,$A66,'S10'!$E$6:$E$13,"Víctor")+SUMIFS('S10'!$I$6:$I$13,'S10'!$B$6:$B$13,$A66,'S10'!$E$6:$E$13,"Ambos")+SUMIFS('Holgura'!$I$6:$I$11,'Holgura'!$B$6:$B$11,$A66,'Holgura'!$E$6:$E$11,"Víctor")+SUMIFS('Holgura'!$I$6:$I$11,'Holgura'!$B$6:$B$11,$A66,'Holgura'!$E$6:$E$11,"Ambos")+SUMIFS('Entrega'!$I$6:$I$9,'Entrega'!$B$6:$B$9,$A66,'Entrega'!$E$6:$E$9,"Víctor")+SUMIFS('Entrega'!$I$6:$I$9,'Entrega'!$B$6:$B$9,$A66,'Entrega'!$E$6:$E$9,"Ambos")+SUMIFS('Defensa'!$I$6:$I$10,'Defensa'!$B$6:$B$10,$A66,'Defensa'!$E$6:$E$10,"Víctor")+SUMIFS('Defensa'!$I$6:$I$10,'Defensa'!$B$6:$B$10,$A66,'Defensa'!$E$6:$E$10,"Ambos")</f>
+        <f>SUMIFS('S1'!$I$6:$I$32,'S1'!$B$6:$B$32,$A66,'S1'!$E$6:$E$32,"Víctor")+SUMIFS('S1'!$I$6:$I$32,'S1'!$B$6:$B$32,$A66,'S1'!$E$6:$E$32,"Ambos")+SUMIFS('S2'!$I$6:$I$23,'S2'!$B$6:$B$23,$A66,'S2'!$E$6:$E$23,"Víctor")+SUMIFS('S2'!$I$6:$I$23,'S2'!$B$6:$B$23,$A66,'S2'!$E$6:$E$23,"Ambos")+SUMIFS('S3'!$I$6:$I$24,'S3'!$B$6:$B$24,$A66,'S3'!$E$6:$E$24,"Víctor")+SUMIFS('S3'!$I$6:$I$24,'S3'!$B$6:$B$24,$A66,'S3'!$E$6:$E$24,"Ambos")+SUMIFS('S4'!$I$6:$I$22,'S4'!$B$6:$B$22,$A66,'S4'!$E$6:$E$22,"Víctor")+SUMIFS('S4'!$I$6:$I$22,'S4'!$B$6:$B$22,$A66,'S4'!$E$6:$E$22,"Ambos")+SUMIFS('S5'!$I$6:$I$20,'S5'!$B$6:$B$20,$A66,'S5'!$E$6:$E$20,"Víctor")+SUMIFS('S5'!$I$6:$I$20,'S5'!$B$6:$B$20,$A66,'S5'!$E$6:$E$20,"Ambos")+SUMIFS('S6'!$I$6:$I$17,'S6'!$B$6:$B$17,$A66,'S6'!$E$6:$E$17,"Víctor")+SUMIFS('S6'!$I$6:$I$17,'S6'!$B$6:$B$17,$A66,'S6'!$E$6:$E$17,"Ambos")+SUMIFS('S7'!$I$6:$I$19,'S7'!$B$6:$B$19,$A66,'S7'!$E$6:$E$19,"Víctor")+SUMIFS('S7'!$I$6:$I$19,'S7'!$B$6:$B$19,$A66,'S7'!$E$6:$E$19,"Ambos")+SUMIFS('S8'!$I$6:$I$23,'S8'!$B$6:$B$23,$A66,'S8'!$E$6:$E$23,"Víctor")+SUMIFS('S8'!$I$6:$I$23,'S8'!$B$6:$B$23,$A66,'S8'!$E$6:$E$23,"Ambos")+SUMIFS('S9'!$I$6:$I$15,'S9'!$B$6:$B$15,$A66,'S9'!$E$6:$E$15,"Víctor")+SUMIFS('S9'!$I$6:$I$15,'S9'!$B$6:$B$15,$A66,'S9'!$E$6:$E$15,"Ambos")+SUMIFS('S10'!$I$6:$I$13,'S10'!$B$6:$B$13,$A66,'S10'!$E$6:$E$13,"Víctor")+SUMIFS('S10'!$I$6:$I$13,'S10'!$B$6:$B$13,$A66,'S10'!$E$6:$E$13,"Ambos")+SUMIFS('Holgura'!$I$6:$I$11,'Holgura'!$B$6:$B$11,$A66,'Holgura'!$E$6:$E$11,"Víctor")+SUMIFS('Holgura'!$I$6:$I$11,'Holgura'!$B$6:$B$11,$A66,'Holgura'!$E$6:$E$11,"Ambos")+SUMIFS('Entrega'!$I$6:$I$9,'Entrega'!$B$6:$B$9,$A66,'Entrega'!$E$6:$E$9,"Víctor")+SUMIFS('Entrega'!$I$6:$I$9,'Entrega'!$B$6:$B$9,$A66,'Entrega'!$E$6:$E$9,"Ambos")+SUMIFS('Defensa'!$I$6:$I$10,'Defensa'!$B$6:$B$10,$A66,'Defensa'!$E$6:$E$10,"Víctor")+SUMIFS('Defensa'!$I$6:$I$10,'Defensa'!$B$6:$B$10,$A66,'Defensa'!$E$6:$E$10,"Ambos")</f>
         <v/>
       </c>
       <c r="E66" s="21">
-        <f>SUMIFS('S1'!$I$6:$I$32,'S1'!$B$6:$B$32,$A66,'S1'!$E$6:$E$32,"Diego")+SUMIFS('S1'!$I$6:$I$32,'S1'!$B$6:$B$32,$A66,'S1'!$E$6:$E$32,"Ambos")+SUMIFS('S2'!$I$6:$I$23,'S2'!$B$6:$B$23,$A66,'S2'!$E$6:$E$23,"Diego")+SUMIFS('S2'!$I$6:$I$23,'S2'!$B$6:$B$23,$A66,'S2'!$E$6:$E$23,"Ambos")+SUMIFS('S3'!$I$6:$I$19,'S3'!$B$6:$B$19,$A66,'S3'!$E$6:$E$19,"Diego")+SUMIFS('S3'!$I$6:$I$19,'S3'!$B$6:$B$19,$A66,'S3'!$E$6:$E$19,"Ambos")+SUMIFS('S4'!$I$6:$I$20,'S4'!$B$6:$B$20,$A66,'S4'!$E$6:$E$20,"Diego")+SUMIFS('S4'!$I$6:$I$20,'S4'!$B$6:$B$20,$A66,'S4'!$E$6:$E$20,"Ambos")+SUMIFS('S5'!$I$6:$I$20,'S5'!$B$6:$B$20,$A66,'S5'!$E$6:$E$20,"Diego")+SUMIFS('S5'!$I$6:$I$20,'S5'!$B$6:$B$20,$A66,'S5'!$E$6:$E$20,"Ambos")+SUMIFS('S6'!$I$6:$I$17,'S6'!$B$6:$B$17,$A66,'S6'!$E$6:$E$17,"Diego")+SUMIFS('S6'!$I$6:$I$17,'S6'!$B$6:$B$17,$A66,'S6'!$E$6:$E$17,"Ambos")+SUMIFS('S7'!$I$6:$I$19,'S7'!$B$6:$B$19,$A66,'S7'!$E$6:$E$19,"Diego")+SUMIFS('S7'!$I$6:$I$19,'S7'!$B$6:$B$19,$A66,'S7'!$E$6:$E$19,"Ambos")+SUMIFS('S8'!$I$6:$I$23,'S8'!$B$6:$B$23,$A66,'S8'!$E$6:$E$23,"Diego")+SUMIFS('S8'!$I$6:$I$23,'S8'!$B$6:$B$23,$A66,'S8'!$E$6:$E$23,"Ambos")+SUMIFS('S9'!$I$6:$I$15,'S9'!$B$6:$B$15,$A66,'S9'!$E$6:$E$15,"Diego")+SUMIFS('S9'!$I$6:$I$15,'S9'!$B$6:$B$15,$A66,'S9'!$E$6:$E$15,"Ambos")+SUMIFS('S10'!$I$6:$I$13,'S10'!$B$6:$B$13,$A66,'S10'!$E$6:$E$13,"Diego")+SUMIFS('S10'!$I$6:$I$13,'S10'!$B$6:$B$13,$A66,'S10'!$E$6:$E$13,"Ambos")+SUMIFS('Holgura'!$I$6:$I$11,'Holgura'!$B$6:$B$11,$A66,'Holgura'!$E$6:$E$11,"Diego")+SUMIFS('Holgura'!$I$6:$I$11,'Holgura'!$B$6:$B$11,$A66,'Holgura'!$E$6:$E$11,"Ambos")+SUMIFS('Entrega'!$I$6:$I$9,'Entrega'!$B$6:$B$9,$A66,'Entrega'!$E$6:$E$9,"Diego")+SUMIFS('Entrega'!$I$6:$I$9,'Entrega'!$B$6:$B$9,$A66,'Entrega'!$E$6:$E$9,"Ambos")+SUMIFS('Defensa'!$I$6:$I$10,'Defensa'!$B$6:$B$10,$A66,'Defensa'!$E$6:$E$10,"Diego")+SUMIFS('Defensa'!$I$6:$I$10,'Defensa'!$B$6:$B$10,$A66,'Defensa'!$E$6:$E$10,"Ambos")</f>
+        <f>SUMIFS('S1'!$I$6:$I$32,'S1'!$B$6:$B$32,$A66,'S1'!$E$6:$E$32,"Diego")+SUMIFS('S1'!$I$6:$I$32,'S1'!$B$6:$B$32,$A66,'S1'!$E$6:$E$32,"Ambos")+SUMIFS('S2'!$I$6:$I$23,'S2'!$B$6:$B$23,$A66,'S2'!$E$6:$E$23,"Diego")+SUMIFS('S2'!$I$6:$I$23,'S2'!$B$6:$B$23,$A66,'S2'!$E$6:$E$23,"Ambos")+SUMIFS('S3'!$I$6:$I$24,'S3'!$B$6:$B$24,$A66,'S3'!$E$6:$E$24,"Diego")+SUMIFS('S3'!$I$6:$I$24,'S3'!$B$6:$B$24,$A66,'S3'!$E$6:$E$24,"Ambos")+SUMIFS('S4'!$I$6:$I$22,'S4'!$B$6:$B$22,$A66,'S4'!$E$6:$E$22,"Diego")+SUMIFS('S4'!$I$6:$I$22,'S4'!$B$6:$B$22,$A66,'S4'!$E$6:$E$22,"Ambos")+SUMIFS('S5'!$I$6:$I$20,'S5'!$B$6:$B$20,$A66,'S5'!$E$6:$E$20,"Diego")+SUMIFS('S5'!$I$6:$I$20,'S5'!$B$6:$B$20,$A66,'S5'!$E$6:$E$20,"Ambos")+SUMIFS('S6'!$I$6:$I$17,'S6'!$B$6:$B$17,$A66,'S6'!$E$6:$E$17,"Diego")+SUMIFS('S6'!$I$6:$I$17,'S6'!$B$6:$B$17,$A66,'S6'!$E$6:$E$17,"Ambos")+SUMIFS('S7'!$I$6:$I$19,'S7'!$B$6:$B$19,$A66,'S7'!$E$6:$E$19,"Diego")+SUMIFS('S7'!$I$6:$I$19,'S7'!$B$6:$B$19,$A66,'S7'!$E$6:$E$19,"Ambos")+SUMIFS('S8'!$I$6:$I$23,'S8'!$B$6:$B$23,$A66,'S8'!$E$6:$E$23,"Diego")+SUMIFS('S8'!$I$6:$I$23,'S8'!$B$6:$B$23,$A66,'S8'!$E$6:$E$23,"Ambos")+SUMIFS('S9'!$I$6:$I$15,'S9'!$B$6:$B$15,$A66,'S9'!$E$6:$E$15,"Diego")+SUMIFS('S9'!$I$6:$I$15,'S9'!$B$6:$B$15,$A66,'S9'!$E$6:$E$15,"Ambos")+SUMIFS('S10'!$I$6:$I$13,'S10'!$B$6:$B$13,$A66,'S10'!$E$6:$E$13,"Diego")+SUMIFS('S10'!$I$6:$I$13,'S10'!$B$6:$B$13,$A66,'S10'!$E$6:$E$13,"Ambos")+SUMIFS('Holgura'!$I$6:$I$11,'Holgura'!$B$6:$B$11,$A66,'Holgura'!$E$6:$E$11,"Diego")+SUMIFS('Holgura'!$I$6:$I$11,'Holgura'!$B$6:$B$11,$A66,'Holgura'!$E$6:$E$11,"Ambos")+SUMIFS('Entrega'!$I$6:$I$9,'Entrega'!$B$6:$B$9,$A66,'Entrega'!$E$6:$E$9,"Diego")+SUMIFS('Entrega'!$I$6:$I$9,'Entrega'!$B$6:$B$9,$A66,'Entrega'!$E$6:$E$9,"Ambos")+SUMIFS('Defensa'!$I$6:$I$10,'Defensa'!$B$6:$B$10,$A66,'Defensa'!$E$6:$E$10,"Diego")+SUMIFS('Defensa'!$I$6:$I$10,'Defensa'!$B$6:$B$10,$A66,'Defensa'!$E$6:$E$10,"Ambos")</f>
         <v/>
       </c>
       <c r="F66" s="21">
-        <f>COUNTIFS('S1'!$B$6:$B$32,$A66,'S1'!$E$6:$E$32,"Víctor")+COUNTIFS('S1'!$B$6:$B$32,$A66,'S1'!$E$6:$E$32,"Ambos")+COUNTIFS('S2'!$B$6:$B$23,$A66,'S2'!$E$6:$E$23,"Víctor")+COUNTIFS('S2'!$B$6:$B$23,$A66,'S2'!$E$6:$E$23,"Ambos")+COUNTIFS('S3'!$B$6:$B$19,$A66,'S3'!$E$6:$E$19,"Víctor")+COUNTIFS('S3'!$B$6:$B$19,$A66,'S3'!$E$6:$E$19,"Ambos")+COUNTIFS('S4'!$B$6:$B$20,$A66,'S4'!$E$6:$E$20,"Víctor")+COUNTIFS('S4'!$B$6:$B$20,$A66,'S4'!$E$6:$E$20,"Ambos")+COUNTIFS('S5'!$B$6:$B$20,$A66,'S5'!$E$6:$E$20,"Víctor")+COUNTIFS('S5'!$B$6:$B$20,$A66,'S5'!$E$6:$E$20,"Ambos")+COUNTIFS('S6'!$B$6:$B$17,$A66,'S6'!$E$6:$E$17,"Víctor")+COUNTIFS('S6'!$B$6:$B$17,$A66,'S6'!$E$6:$E$17,"Ambos")+COUNTIFS('S7'!$B$6:$B$19,$A66,'S7'!$E$6:$E$19,"Víctor")+COUNTIFS('S7'!$B$6:$B$19,$A66,'S7'!$E$6:$E$19,"Ambos")+COUNTIFS('S8'!$B$6:$B$23,$A66,'S8'!$E$6:$E$23,"Víctor")+COUNTIFS('S8'!$B$6:$B$23,$A66,'S8'!$E$6:$E$23,"Ambos")+COUNTIFS('S9'!$B$6:$B$15,$A66,'S9'!$E$6:$E$15,"Víctor")+COUNTIFS('S9'!$B$6:$B$15,$A66,'S9'!$E$6:$E$15,"Ambos")+COUNTIFS('S10'!$B$6:$B$13,$A66,'S10'!$E$6:$E$13,"Víctor")+COUNTIFS('S10'!$B$6:$B$13,$A66,'S10'!$E$6:$E$13,"Ambos")+COUNTIFS('Holgura'!$B$6:$B$11,$A66,'Holgura'!$E$6:$E$11,"Víctor")+COUNTIFS('Holgura'!$B$6:$B$11,$A66,'Holgura'!$E$6:$E$11,"Ambos")+COUNTIFS('Entrega'!$B$6:$B$9,$A66,'Entrega'!$E$6:$E$9,"Víctor")+COUNTIFS('Entrega'!$B$6:$B$9,$A66,'Entrega'!$E$6:$E$9,"Ambos")+COUNTIFS('Defensa'!$B$6:$B$10,$A66,'Defensa'!$E$6:$E$10,"Víctor")+COUNTIFS('Defensa'!$B$6:$B$10,$A66,'Defensa'!$E$6:$E$10,"Ambos")</f>
+        <f>COUNTIFS('S1'!$B$6:$B$32,$A66,'S1'!$E$6:$E$32,"Víctor")+COUNTIFS('S1'!$B$6:$B$32,$A66,'S1'!$E$6:$E$32,"Ambos")+COUNTIFS('S2'!$B$6:$B$23,$A66,'S2'!$E$6:$E$23,"Víctor")+COUNTIFS('S2'!$B$6:$B$23,$A66,'S2'!$E$6:$E$23,"Ambos")+COUNTIFS('S3'!$B$6:$B$24,$A66,'S3'!$E$6:$E$24,"Víctor")+COUNTIFS('S3'!$B$6:$B$24,$A66,'S3'!$E$6:$E$24,"Ambos")+COUNTIFS('S4'!$B$6:$B$22,$A66,'S4'!$E$6:$E$22,"Víctor")+COUNTIFS('S4'!$B$6:$B$22,$A66,'S4'!$E$6:$E$22,"Ambos")+COUNTIFS('S5'!$B$6:$B$20,$A66,'S5'!$E$6:$E$20,"Víctor")+COUNTIFS('S5'!$B$6:$B$20,$A66,'S5'!$E$6:$E$20,"Ambos")+COUNTIFS('S6'!$B$6:$B$17,$A66,'S6'!$E$6:$E$17,"Víctor")+COUNTIFS('S6'!$B$6:$B$17,$A66,'S6'!$E$6:$E$17,"Ambos")+COUNTIFS('S7'!$B$6:$B$19,$A66,'S7'!$E$6:$E$19,"Víctor")+COUNTIFS('S7'!$B$6:$B$19,$A66,'S7'!$E$6:$E$19,"Ambos")+COUNTIFS('S8'!$B$6:$B$23,$A66,'S8'!$E$6:$E$23,"Víctor")+COUNTIFS('S8'!$B$6:$B$23,$A66,'S8'!$E$6:$E$23,"Ambos")+COUNTIFS('S9'!$B$6:$B$15,$A66,'S9'!$E$6:$E$15,"Víctor")+COUNTIFS('S9'!$B$6:$B$15,$A66,'S9'!$E$6:$E$15,"Ambos")+COUNTIFS('S10'!$B$6:$B$13,$A66,'S10'!$E$6:$E$13,"Víctor")+COUNTIFS('S10'!$B$6:$B$13,$A66,'S10'!$E$6:$E$13,"Ambos")+COUNTIFS('Holgura'!$B$6:$B$11,$A66,'Holgura'!$E$6:$E$11,"Víctor")+COUNTIFS('Holgura'!$B$6:$B$11,$A66,'Holgura'!$E$6:$E$11,"Ambos")+COUNTIFS('Entrega'!$B$6:$B$9,$A66,'Entrega'!$E$6:$E$9,"Víctor")+COUNTIFS('Entrega'!$B$6:$B$9,$A66,'Entrega'!$E$6:$E$9,"Ambos")+COUNTIFS('Defensa'!$B$6:$B$10,$A66,'Defensa'!$E$6:$E$10,"Víctor")+COUNTIFS('Defensa'!$B$6:$B$10,$A66,'Defensa'!$E$6:$E$10,"Ambos")</f>
         <v/>
       </c>
       <c r="G66" s="21">
-        <f>COUNTIFS('S1'!$B$6:$B$32,$A66,'S1'!$E$6:$E$32,"Diego")+COUNTIFS('S1'!$B$6:$B$32,$A66,'S1'!$E$6:$E$32,"Ambos")+COUNTIFS('S2'!$B$6:$B$23,$A66,'S2'!$E$6:$E$23,"Diego")+COUNTIFS('S2'!$B$6:$B$23,$A66,'S2'!$E$6:$E$23,"Ambos")+COUNTIFS('S3'!$B$6:$B$19,$A66,'S3'!$E$6:$E$19,"Diego")+COUNTIFS('S3'!$B$6:$B$19,$A66,'S3'!$E$6:$E$19,"Ambos")+COUNTIFS('S4'!$B$6:$B$20,$A66,'S4'!$E$6:$E$20,"Diego")+COUNTIFS('S4'!$B$6:$B$20,$A66,'S4'!$E$6:$E$20,"Ambos")+COUNTIFS('S5'!$B$6:$B$20,$A66,'S5'!$E$6:$E$20,"Diego")+COUNTIFS('S5'!$B$6:$B$20,$A66,'S5'!$E$6:$E$20,"Ambos")+COUNTIFS('S6'!$B$6:$B$17,$A66,'S6'!$E$6:$E$17,"Diego")+COUNTIFS('S6'!$B$6:$B$17,$A66,'S6'!$E$6:$E$17,"Ambos")+COUNTIFS('S7'!$B$6:$B$19,$A66,'S7'!$E$6:$E$19,"Diego")+COUNTIFS('S7'!$B$6:$B$19,$A66,'S7'!$E$6:$E$19,"Ambos")+COUNTIFS('S8'!$B$6:$B$23,$A66,'S8'!$E$6:$E$23,"Diego")+COUNTIFS('S8'!$B$6:$B$23,$A66,'S8'!$E$6:$E$23,"Ambos")+COUNTIFS('S9'!$B$6:$B$15,$A66,'S9'!$E$6:$E$15,"Diego")+COUNTIFS('S9'!$B$6:$B$15,$A66,'S9'!$E$6:$E$15,"Ambos")+COUNTIFS('S10'!$B$6:$B$13,$A66,'S10'!$E$6:$E$13,"Diego")+COUNTIFS('S10'!$B$6:$B$13,$A66,'S10'!$E$6:$E$13,"Ambos")+COUNTIFS('Holgura'!$B$6:$B$11,$A66,'Holgura'!$E$6:$E$11,"Diego")+COUNTIFS('Holgura'!$B$6:$B$11,$A66,'Holgura'!$E$6:$E$11,"Ambos")+COUNTIFS('Entrega'!$B$6:$B$9,$A66,'Entrega'!$E$6:$E$9,"Diego")+COUNTIFS('Entrega'!$B$6:$B$9,$A66,'Entrega'!$E$6:$E$9,"Ambos")+COUNTIFS('Defensa'!$B$6:$B$10,$A66,'Defensa'!$E$6:$E$10,"Diego")+COUNTIFS('Defensa'!$B$6:$B$10,$A66,'Defensa'!$E$6:$E$10,"Ambos")</f>
+        <f>COUNTIFS('S1'!$B$6:$B$32,$A66,'S1'!$E$6:$E$32,"Diego")+COUNTIFS('S1'!$B$6:$B$32,$A66,'S1'!$E$6:$E$32,"Ambos")+COUNTIFS('S2'!$B$6:$B$23,$A66,'S2'!$E$6:$E$23,"Diego")+COUNTIFS('S2'!$B$6:$B$23,$A66,'S2'!$E$6:$E$23,"Ambos")+COUNTIFS('S3'!$B$6:$B$24,$A66,'S3'!$E$6:$E$24,"Diego")+COUNTIFS('S3'!$B$6:$B$24,$A66,'S3'!$E$6:$E$24,"Ambos")+COUNTIFS('S4'!$B$6:$B$22,$A66,'S4'!$E$6:$E$22,"Diego")+COUNTIFS('S4'!$B$6:$B$22,$A66,'S4'!$E$6:$E$22,"Ambos")+COUNTIFS('S5'!$B$6:$B$20,$A66,'S5'!$E$6:$E$20,"Diego")+COUNTIFS('S5'!$B$6:$B$20,$A66,'S5'!$E$6:$E$20,"Ambos")+COUNTIFS('S6'!$B$6:$B$17,$A66,'S6'!$E$6:$E$17,"Diego")+COUNTIFS('S6'!$B$6:$B$17,$A66,'S6'!$E$6:$E$17,"Ambos")+COUNTIFS('S7'!$B$6:$B$19,$A66,'S7'!$E$6:$E$19,"Diego")+COUNTIFS('S7'!$B$6:$B$19,$A66,'S7'!$E$6:$E$19,"Ambos")+COUNTIFS('S8'!$B$6:$B$23,$A66,'S8'!$E$6:$E$23,"Diego")+COUNTIFS('S8'!$B$6:$B$23,$A66,'S8'!$E$6:$E$23,"Ambos")+COUNTIFS('S9'!$B$6:$B$15,$A66,'S9'!$E$6:$E$15,"Diego")+COUNTIFS('S9'!$B$6:$B$15,$A66,'S9'!$E$6:$E$15,"Ambos")+COUNTIFS('S10'!$B$6:$B$13,$A66,'S10'!$E$6:$E$13,"Diego")+COUNTIFS('S10'!$B$6:$B$13,$A66,'S10'!$E$6:$E$13,"Ambos")+COUNTIFS('Holgura'!$B$6:$B$11,$A66,'Holgura'!$E$6:$E$11,"Diego")+COUNTIFS('Holgura'!$B$6:$B$11,$A66,'Holgura'!$E$6:$E$11,"Ambos")+COUNTIFS('Entrega'!$B$6:$B$9,$A66,'Entrega'!$E$6:$E$9,"Diego")+COUNTIFS('Entrega'!$B$6:$B$9,$A66,'Entrega'!$E$6:$E$9,"Ambos")+COUNTIFS('Defensa'!$B$6:$B$10,$A66,'Defensa'!$E$6:$E$10,"Diego")+COUNTIFS('Defensa'!$B$6:$B$10,$A66,'Defensa'!$E$6:$E$10,"Ambos")</f>
         <v/>
       </c>
     </row>
@@ -10478,19 +10499,19 @@
         <v/>
       </c>
       <c r="D67" s="21">
-        <f>SUMIFS('S1'!$I$6:$I$32,'S1'!$B$6:$B$32,$A67,'S1'!$E$6:$E$32,"Víctor")+SUMIFS('S1'!$I$6:$I$32,'S1'!$B$6:$B$32,$A67,'S1'!$E$6:$E$32,"Ambos")+SUMIFS('S2'!$I$6:$I$23,'S2'!$B$6:$B$23,$A67,'S2'!$E$6:$E$23,"Víctor")+SUMIFS('S2'!$I$6:$I$23,'S2'!$B$6:$B$23,$A67,'S2'!$E$6:$E$23,"Ambos")+SUMIFS('S3'!$I$6:$I$19,'S3'!$B$6:$B$19,$A67,'S3'!$E$6:$E$19,"Víctor")+SUMIFS('S3'!$I$6:$I$19,'S3'!$B$6:$B$19,$A67,'S3'!$E$6:$E$19,"Ambos")+SUMIFS('S4'!$I$6:$I$20,'S4'!$B$6:$B$20,$A67,'S4'!$E$6:$E$20,"Víctor")+SUMIFS('S4'!$I$6:$I$20,'S4'!$B$6:$B$20,$A67,'S4'!$E$6:$E$20,"Ambos")+SUMIFS('S5'!$I$6:$I$20,'S5'!$B$6:$B$20,$A67,'S5'!$E$6:$E$20,"Víctor")+SUMIFS('S5'!$I$6:$I$20,'S5'!$B$6:$B$20,$A67,'S5'!$E$6:$E$20,"Ambos")+SUMIFS('S6'!$I$6:$I$17,'S6'!$B$6:$B$17,$A67,'S6'!$E$6:$E$17,"Víctor")+SUMIFS('S6'!$I$6:$I$17,'S6'!$B$6:$B$17,$A67,'S6'!$E$6:$E$17,"Ambos")+SUMIFS('S7'!$I$6:$I$19,'S7'!$B$6:$B$19,$A67,'S7'!$E$6:$E$19,"Víctor")+SUMIFS('S7'!$I$6:$I$19,'S7'!$B$6:$B$19,$A67,'S7'!$E$6:$E$19,"Ambos")+SUMIFS('S8'!$I$6:$I$23,'S8'!$B$6:$B$23,$A67,'S8'!$E$6:$E$23,"Víctor")+SUMIFS('S8'!$I$6:$I$23,'S8'!$B$6:$B$23,$A67,'S8'!$E$6:$E$23,"Ambos")+SUMIFS('S9'!$I$6:$I$15,'S9'!$B$6:$B$15,$A67,'S9'!$E$6:$E$15,"Víctor")+SUMIFS('S9'!$I$6:$I$15,'S9'!$B$6:$B$15,$A67,'S9'!$E$6:$E$15,"Ambos")+SUMIFS('S10'!$I$6:$I$13,'S10'!$B$6:$B$13,$A67,'S10'!$E$6:$E$13,"Víctor")+SUMIFS('S10'!$I$6:$I$13,'S10'!$B$6:$B$13,$A67,'S10'!$E$6:$E$13,"Ambos")+SUMIFS('Holgura'!$I$6:$I$11,'Holgura'!$B$6:$B$11,$A67,'Holgura'!$E$6:$E$11,"Víctor")+SUMIFS('Holgura'!$I$6:$I$11,'Holgura'!$B$6:$B$11,$A67,'Holgura'!$E$6:$E$11,"Ambos")+SUMIFS('Entrega'!$I$6:$I$9,'Entrega'!$B$6:$B$9,$A67,'Entrega'!$E$6:$E$9,"Víctor")+SUMIFS('Entrega'!$I$6:$I$9,'Entrega'!$B$6:$B$9,$A67,'Entrega'!$E$6:$E$9,"Ambos")+SUMIFS('Defensa'!$I$6:$I$10,'Defensa'!$B$6:$B$10,$A67,'Defensa'!$E$6:$E$10,"Víctor")+SUMIFS('Defensa'!$I$6:$I$10,'Defensa'!$B$6:$B$10,$A67,'Defensa'!$E$6:$E$10,"Ambos")</f>
+        <f>SUMIFS('S1'!$I$6:$I$32,'S1'!$B$6:$B$32,$A67,'S1'!$E$6:$E$32,"Víctor")+SUMIFS('S1'!$I$6:$I$32,'S1'!$B$6:$B$32,$A67,'S1'!$E$6:$E$32,"Ambos")+SUMIFS('S2'!$I$6:$I$23,'S2'!$B$6:$B$23,$A67,'S2'!$E$6:$E$23,"Víctor")+SUMIFS('S2'!$I$6:$I$23,'S2'!$B$6:$B$23,$A67,'S2'!$E$6:$E$23,"Ambos")+SUMIFS('S3'!$I$6:$I$24,'S3'!$B$6:$B$24,$A67,'S3'!$E$6:$E$24,"Víctor")+SUMIFS('S3'!$I$6:$I$24,'S3'!$B$6:$B$24,$A67,'S3'!$E$6:$E$24,"Ambos")+SUMIFS('S4'!$I$6:$I$22,'S4'!$B$6:$B$22,$A67,'S4'!$E$6:$E$22,"Víctor")+SUMIFS('S4'!$I$6:$I$22,'S4'!$B$6:$B$22,$A67,'S4'!$E$6:$E$22,"Ambos")+SUMIFS('S5'!$I$6:$I$20,'S5'!$B$6:$B$20,$A67,'S5'!$E$6:$E$20,"Víctor")+SUMIFS('S5'!$I$6:$I$20,'S5'!$B$6:$B$20,$A67,'S5'!$E$6:$E$20,"Ambos")+SUMIFS('S6'!$I$6:$I$17,'S6'!$B$6:$B$17,$A67,'S6'!$E$6:$E$17,"Víctor")+SUMIFS('S6'!$I$6:$I$17,'S6'!$B$6:$B$17,$A67,'S6'!$E$6:$E$17,"Ambos")+SUMIFS('S7'!$I$6:$I$19,'S7'!$B$6:$B$19,$A67,'S7'!$E$6:$E$19,"Víctor")+SUMIFS('S7'!$I$6:$I$19,'S7'!$B$6:$B$19,$A67,'S7'!$E$6:$E$19,"Ambos")+SUMIFS('S8'!$I$6:$I$23,'S8'!$B$6:$B$23,$A67,'S8'!$E$6:$E$23,"Víctor")+SUMIFS('S8'!$I$6:$I$23,'S8'!$B$6:$B$23,$A67,'S8'!$E$6:$E$23,"Ambos")+SUMIFS('S9'!$I$6:$I$15,'S9'!$B$6:$B$15,$A67,'S9'!$E$6:$E$15,"Víctor")+SUMIFS('S9'!$I$6:$I$15,'S9'!$B$6:$B$15,$A67,'S9'!$E$6:$E$15,"Ambos")+SUMIFS('S10'!$I$6:$I$13,'S10'!$B$6:$B$13,$A67,'S10'!$E$6:$E$13,"Víctor")+SUMIFS('S10'!$I$6:$I$13,'S10'!$B$6:$B$13,$A67,'S10'!$E$6:$E$13,"Ambos")+SUMIFS('Holgura'!$I$6:$I$11,'Holgura'!$B$6:$B$11,$A67,'Holgura'!$E$6:$E$11,"Víctor")+SUMIFS('Holgura'!$I$6:$I$11,'Holgura'!$B$6:$B$11,$A67,'Holgura'!$E$6:$E$11,"Ambos")+SUMIFS('Entrega'!$I$6:$I$9,'Entrega'!$B$6:$B$9,$A67,'Entrega'!$E$6:$E$9,"Víctor")+SUMIFS('Entrega'!$I$6:$I$9,'Entrega'!$B$6:$B$9,$A67,'Entrega'!$E$6:$E$9,"Ambos")+SUMIFS('Defensa'!$I$6:$I$10,'Defensa'!$B$6:$B$10,$A67,'Defensa'!$E$6:$E$10,"Víctor")+SUMIFS('Defensa'!$I$6:$I$10,'Defensa'!$B$6:$B$10,$A67,'Defensa'!$E$6:$E$10,"Ambos")</f>
         <v/>
       </c>
       <c r="E67" s="21">
-        <f>SUMIFS('S1'!$I$6:$I$32,'S1'!$B$6:$B$32,$A67,'S1'!$E$6:$E$32,"Diego")+SUMIFS('S1'!$I$6:$I$32,'S1'!$B$6:$B$32,$A67,'S1'!$E$6:$E$32,"Ambos")+SUMIFS('S2'!$I$6:$I$23,'S2'!$B$6:$B$23,$A67,'S2'!$E$6:$E$23,"Diego")+SUMIFS('S2'!$I$6:$I$23,'S2'!$B$6:$B$23,$A67,'S2'!$E$6:$E$23,"Ambos")+SUMIFS('S3'!$I$6:$I$19,'S3'!$B$6:$B$19,$A67,'S3'!$E$6:$E$19,"Diego")+SUMIFS('S3'!$I$6:$I$19,'S3'!$B$6:$B$19,$A67,'S3'!$E$6:$E$19,"Ambos")+SUMIFS('S4'!$I$6:$I$20,'S4'!$B$6:$B$20,$A67,'S4'!$E$6:$E$20,"Diego")+SUMIFS('S4'!$I$6:$I$20,'S4'!$B$6:$B$20,$A67,'S4'!$E$6:$E$20,"Ambos")+SUMIFS('S5'!$I$6:$I$20,'S5'!$B$6:$B$20,$A67,'S5'!$E$6:$E$20,"Diego")+SUMIFS('S5'!$I$6:$I$20,'S5'!$B$6:$B$20,$A67,'S5'!$E$6:$E$20,"Ambos")+SUMIFS('S6'!$I$6:$I$17,'S6'!$B$6:$B$17,$A67,'S6'!$E$6:$E$17,"Diego")+SUMIFS('S6'!$I$6:$I$17,'S6'!$B$6:$B$17,$A67,'S6'!$E$6:$E$17,"Ambos")+SUMIFS('S7'!$I$6:$I$19,'S7'!$B$6:$B$19,$A67,'S7'!$E$6:$E$19,"Diego")+SUMIFS('S7'!$I$6:$I$19,'S7'!$B$6:$B$19,$A67,'S7'!$E$6:$E$19,"Ambos")+SUMIFS('S8'!$I$6:$I$23,'S8'!$B$6:$B$23,$A67,'S8'!$E$6:$E$23,"Diego")+SUMIFS('S8'!$I$6:$I$23,'S8'!$B$6:$B$23,$A67,'S8'!$E$6:$E$23,"Ambos")+SUMIFS('S9'!$I$6:$I$15,'S9'!$B$6:$B$15,$A67,'S9'!$E$6:$E$15,"Diego")+SUMIFS('S9'!$I$6:$I$15,'S9'!$B$6:$B$15,$A67,'S9'!$E$6:$E$15,"Ambos")+SUMIFS('S10'!$I$6:$I$13,'S10'!$B$6:$B$13,$A67,'S10'!$E$6:$E$13,"Diego")+SUMIFS('S10'!$I$6:$I$13,'S10'!$B$6:$B$13,$A67,'S10'!$E$6:$E$13,"Ambos")+SUMIFS('Holgura'!$I$6:$I$11,'Holgura'!$B$6:$B$11,$A67,'Holgura'!$E$6:$E$11,"Diego")+SUMIFS('Holgura'!$I$6:$I$11,'Holgura'!$B$6:$B$11,$A67,'Holgura'!$E$6:$E$11,"Ambos")+SUMIFS('Entrega'!$I$6:$I$9,'Entrega'!$B$6:$B$9,$A67,'Entrega'!$E$6:$E$9,"Diego")+SUMIFS('Entrega'!$I$6:$I$9,'Entrega'!$B$6:$B$9,$A67,'Entrega'!$E$6:$E$9,"Ambos")+SUMIFS('Defensa'!$I$6:$I$10,'Defensa'!$B$6:$B$10,$A67,'Defensa'!$E$6:$E$10,"Diego")+SUMIFS('Defensa'!$I$6:$I$10,'Defensa'!$B$6:$B$10,$A67,'Defensa'!$E$6:$E$10,"Ambos")</f>
+        <f>SUMIFS('S1'!$I$6:$I$32,'S1'!$B$6:$B$32,$A67,'S1'!$E$6:$E$32,"Diego")+SUMIFS('S1'!$I$6:$I$32,'S1'!$B$6:$B$32,$A67,'S1'!$E$6:$E$32,"Ambos")+SUMIFS('S2'!$I$6:$I$23,'S2'!$B$6:$B$23,$A67,'S2'!$E$6:$E$23,"Diego")+SUMIFS('S2'!$I$6:$I$23,'S2'!$B$6:$B$23,$A67,'S2'!$E$6:$E$23,"Ambos")+SUMIFS('S3'!$I$6:$I$24,'S3'!$B$6:$B$24,$A67,'S3'!$E$6:$E$24,"Diego")+SUMIFS('S3'!$I$6:$I$24,'S3'!$B$6:$B$24,$A67,'S3'!$E$6:$E$24,"Ambos")+SUMIFS('S4'!$I$6:$I$22,'S4'!$B$6:$B$22,$A67,'S4'!$E$6:$E$22,"Diego")+SUMIFS('S4'!$I$6:$I$22,'S4'!$B$6:$B$22,$A67,'S4'!$E$6:$E$22,"Ambos")+SUMIFS('S5'!$I$6:$I$20,'S5'!$B$6:$B$20,$A67,'S5'!$E$6:$E$20,"Diego")+SUMIFS('S5'!$I$6:$I$20,'S5'!$B$6:$B$20,$A67,'S5'!$E$6:$E$20,"Ambos")+SUMIFS('S6'!$I$6:$I$17,'S6'!$B$6:$B$17,$A67,'S6'!$E$6:$E$17,"Diego")+SUMIFS('S6'!$I$6:$I$17,'S6'!$B$6:$B$17,$A67,'S6'!$E$6:$E$17,"Ambos")+SUMIFS('S7'!$I$6:$I$19,'S7'!$B$6:$B$19,$A67,'S7'!$E$6:$E$19,"Diego")+SUMIFS('S7'!$I$6:$I$19,'S7'!$B$6:$B$19,$A67,'S7'!$E$6:$E$19,"Ambos")+SUMIFS('S8'!$I$6:$I$23,'S8'!$B$6:$B$23,$A67,'S8'!$E$6:$E$23,"Diego")+SUMIFS('S8'!$I$6:$I$23,'S8'!$B$6:$B$23,$A67,'S8'!$E$6:$E$23,"Ambos")+SUMIFS('S9'!$I$6:$I$15,'S9'!$B$6:$B$15,$A67,'S9'!$E$6:$E$15,"Diego")+SUMIFS('S9'!$I$6:$I$15,'S9'!$B$6:$B$15,$A67,'S9'!$E$6:$E$15,"Ambos")+SUMIFS('S10'!$I$6:$I$13,'S10'!$B$6:$B$13,$A67,'S10'!$E$6:$E$13,"Diego")+SUMIFS('S10'!$I$6:$I$13,'S10'!$B$6:$B$13,$A67,'S10'!$E$6:$E$13,"Ambos")+SUMIFS('Holgura'!$I$6:$I$11,'Holgura'!$B$6:$B$11,$A67,'Holgura'!$E$6:$E$11,"Diego")+SUMIFS('Holgura'!$I$6:$I$11,'Holgura'!$B$6:$B$11,$A67,'Holgura'!$E$6:$E$11,"Ambos")+SUMIFS('Entrega'!$I$6:$I$9,'Entrega'!$B$6:$B$9,$A67,'Entrega'!$E$6:$E$9,"Diego")+SUMIFS('Entrega'!$I$6:$I$9,'Entrega'!$B$6:$B$9,$A67,'Entrega'!$E$6:$E$9,"Ambos")+SUMIFS('Defensa'!$I$6:$I$10,'Defensa'!$B$6:$B$10,$A67,'Defensa'!$E$6:$E$10,"Diego")+SUMIFS('Defensa'!$I$6:$I$10,'Defensa'!$B$6:$B$10,$A67,'Defensa'!$E$6:$E$10,"Ambos")</f>
         <v/>
       </c>
       <c r="F67" s="21">
-        <f>COUNTIFS('S1'!$B$6:$B$32,$A67,'S1'!$E$6:$E$32,"Víctor")+COUNTIFS('S1'!$B$6:$B$32,$A67,'S1'!$E$6:$E$32,"Ambos")+COUNTIFS('S2'!$B$6:$B$23,$A67,'S2'!$E$6:$E$23,"Víctor")+COUNTIFS('S2'!$B$6:$B$23,$A67,'S2'!$E$6:$E$23,"Ambos")+COUNTIFS('S3'!$B$6:$B$19,$A67,'S3'!$E$6:$E$19,"Víctor")+COUNTIFS('S3'!$B$6:$B$19,$A67,'S3'!$E$6:$E$19,"Ambos")+COUNTIFS('S4'!$B$6:$B$20,$A67,'S4'!$E$6:$E$20,"Víctor")+COUNTIFS('S4'!$B$6:$B$20,$A67,'S4'!$E$6:$E$20,"Ambos")+COUNTIFS('S5'!$B$6:$B$20,$A67,'S5'!$E$6:$E$20,"Víctor")+COUNTIFS('S5'!$B$6:$B$20,$A67,'S5'!$E$6:$E$20,"Ambos")+COUNTIFS('S6'!$B$6:$B$17,$A67,'S6'!$E$6:$E$17,"Víctor")+COUNTIFS('S6'!$B$6:$B$17,$A67,'S6'!$E$6:$E$17,"Ambos")+COUNTIFS('S7'!$B$6:$B$19,$A67,'S7'!$E$6:$E$19,"Víctor")+COUNTIFS('S7'!$B$6:$B$19,$A67,'S7'!$E$6:$E$19,"Ambos")+COUNTIFS('S8'!$B$6:$B$23,$A67,'S8'!$E$6:$E$23,"Víctor")+COUNTIFS('S8'!$B$6:$B$23,$A67,'S8'!$E$6:$E$23,"Ambos")+COUNTIFS('S9'!$B$6:$B$15,$A67,'S9'!$E$6:$E$15,"Víctor")+COUNTIFS('S9'!$B$6:$B$15,$A67,'S9'!$E$6:$E$15,"Ambos")+COUNTIFS('S10'!$B$6:$B$13,$A67,'S10'!$E$6:$E$13,"Víctor")+COUNTIFS('S10'!$B$6:$B$13,$A67,'S10'!$E$6:$E$13,"Ambos")+COUNTIFS('Holgura'!$B$6:$B$11,$A67,'Holgura'!$E$6:$E$11,"Víctor")+COUNTIFS('Holgura'!$B$6:$B$11,$A67,'Holgura'!$E$6:$E$11,"Ambos")+COUNTIFS('Entrega'!$B$6:$B$9,$A67,'Entrega'!$E$6:$E$9,"Víctor")+COUNTIFS('Entrega'!$B$6:$B$9,$A67,'Entrega'!$E$6:$E$9,"Ambos")+COUNTIFS('Defensa'!$B$6:$B$10,$A67,'Defensa'!$E$6:$E$10,"Víctor")+COUNTIFS('Defensa'!$B$6:$B$10,$A67,'Defensa'!$E$6:$E$10,"Ambos")</f>
+        <f>COUNTIFS('S1'!$B$6:$B$32,$A67,'S1'!$E$6:$E$32,"Víctor")+COUNTIFS('S1'!$B$6:$B$32,$A67,'S1'!$E$6:$E$32,"Ambos")+COUNTIFS('S2'!$B$6:$B$23,$A67,'S2'!$E$6:$E$23,"Víctor")+COUNTIFS('S2'!$B$6:$B$23,$A67,'S2'!$E$6:$E$23,"Ambos")+COUNTIFS('S3'!$B$6:$B$24,$A67,'S3'!$E$6:$E$24,"Víctor")+COUNTIFS('S3'!$B$6:$B$24,$A67,'S3'!$E$6:$E$24,"Ambos")+COUNTIFS('S4'!$B$6:$B$22,$A67,'S4'!$E$6:$E$22,"Víctor")+COUNTIFS('S4'!$B$6:$B$22,$A67,'S4'!$E$6:$E$22,"Ambos")+COUNTIFS('S5'!$B$6:$B$20,$A67,'S5'!$E$6:$E$20,"Víctor")+COUNTIFS('S5'!$B$6:$B$20,$A67,'S5'!$E$6:$E$20,"Ambos")+COUNTIFS('S6'!$B$6:$B$17,$A67,'S6'!$E$6:$E$17,"Víctor")+COUNTIFS('S6'!$B$6:$B$17,$A67,'S6'!$E$6:$E$17,"Ambos")+COUNTIFS('S7'!$B$6:$B$19,$A67,'S7'!$E$6:$E$19,"Víctor")+COUNTIFS('S7'!$B$6:$B$19,$A67,'S7'!$E$6:$E$19,"Ambos")+COUNTIFS('S8'!$B$6:$B$23,$A67,'S8'!$E$6:$E$23,"Víctor")+COUNTIFS('S8'!$B$6:$B$23,$A67,'S8'!$E$6:$E$23,"Ambos")+COUNTIFS('S9'!$B$6:$B$15,$A67,'S9'!$E$6:$E$15,"Víctor")+COUNTIFS('S9'!$B$6:$B$15,$A67,'S9'!$E$6:$E$15,"Ambos")+COUNTIFS('S10'!$B$6:$B$13,$A67,'S10'!$E$6:$E$13,"Víctor")+COUNTIFS('S10'!$B$6:$B$13,$A67,'S10'!$E$6:$E$13,"Ambos")+COUNTIFS('Holgura'!$B$6:$B$11,$A67,'Holgura'!$E$6:$E$11,"Víctor")+COUNTIFS('Holgura'!$B$6:$B$11,$A67,'Holgura'!$E$6:$E$11,"Ambos")+COUNTIFS('Entrega'!$B$6:$B$9,$A67,'Entrega'!$E$6:$E$9,"Víctor")+COUNTIFS('Entrega'!$B$6:$B$9,$A67,'Entrega'!$E$6:$E$9,"Ambos")+COUNTIFS('Defensa'!$B$6:$B$10,$A67,'Defensa'!$E$6:$E$10,"Víctor")+COUNTIFS('Defensa'!$B$6:$B$10,$A67,'Defensa'!$E$6:$E$10,"Ambos")</f>
         <v/>
       </c>
       <c r="G67" s="21">
-        <f>COUNTIFS('S1'!$B$6:$B$32,$A67,'S1'!$E$6:$E$32,"Diego")+COUNTIFS('S1'!$B$6:$B$32,$A67,'S1'!$E$6:$E$32,"Ambos")+COUNTIFS('S2'!$B$6:$B$23,$A67,'S2'!$E$6:$E$23,"Diego")+COUNTIFS('S2'!$B$6:$B$23,$A67,'S2'!$E$6:$E$23,"Ambos")+COUNTIFS('S3'!$B$6:$B$19,$A67,'S3'!$E$6:$E$19,"Diego")+COUNTIFS('S3'!$B$6:$B$19,$A67,'S3'!$E$6:$E$19,"Ambos")+COUNTIFS('S4'!$B$6:$B$20,$A67,'S4'!$E$6:$E$20,"Diego")+COUNTIFS('S4'!$B$6:$B$20,$A67,'S4'!$E$6:$E$20,"Ambos")+COUNTIFS('S5'!$B$6:$B$20,$A67,'S5'!$E$6:$E$20,"Diego")+COUNTIFS('S5'!$B$6:$B$20,$A67,'S5'!$E$6:$E$20,"Ambos")+COUNTIFS('S6'!$B$6:$B$17,$A67,'S6'!$E$6:$E$17,"Diego")+COUNTIFS('S6'!$B$6:$B$17,$A67,'S6'!$E$6:$E$17,"Ambos")+COUNTIFS('S7'!$B$6:$B$19,$A67,'S7'!$E$6:$E$19,"Diego")+COUNTIFS('S7'!$B$6:$B$19,$A67,'S7'!$E$6:$E$19,"Ambos")+COUNTIFS('S8'!$B$6:$B$23,$A67,'S8'!$E$6:$E$23,"Diego")+COUNTIFS('S8'!$B$6:$B$23,$A67,'S8'!$E$6:$E$23,"Ambos")+COUNTIFS('S9'!$B$6:$B$15,$A67,'S9'!$E$6:$E$15,"Diego")+COUNTIFS('S9'!$B$6:$B$15,$A67,'S9'!$E$6:$E$15,"Ambos")+COUNTIFS('S10'!$B$6:$B$13,$A67,'S10'!$E$6:$E$13,"Diego")+COUNTIFS('S10'!$B$6:$B$13,$A67,'S10'!$E$6:$E$13,"Ambos")+COUNTIFS('Holgura'!$B$6:$B$11,$A67,'Holgura'!$E$6:$E$11,"Diego")+COUNTIFS('Holgura'!$B$6:$B$11,$A67,'Holgura'!$E$6:$E$11,"Ambos")+COUNTIFS('Entrega'!$B$6:$B$9,$A67,'Entrega'!$E$6:$E$9,"Diego")+COUNTIFS('Entrega'!$B$6:$B$9,$A67,'Entrega'!$E$6:$E$9,"Ambos")+COUNTIFS('Defensa'!$B$6:$B$10,$A67,'Defensa'!$E$6:$E$10,"Diego")+COUNTIFS('Defensa'!$B$6:$B$10,$A67,'Defensa'!$E$6:$E$10,"Ambos")</f>
+        <f>COUNTIFS('S1'!$B$6:$B$32,$A67,'S1'!$E$6:$E$32,"Diego")+COUNTIFS('S1'!$B$6:$B$32,$A67,'S1'!$E$6:$E$32,"Ambos")+COUNTIFS('S2'!$B$6:$B$23,$A67,'S2'!$E$6:$E$23,"Diego")+COUNTIFS('S2'!$B$6:$B$23,$A67,'S2'!$E$6:$E$23,"Ambos")+COUNTIFS('S3'!$B$6:$B$24,$A67,'S3'!$E$6:$E$24,"Diego")+COUNTIFS('S3'!$B$6:$B$24,$A67,'S3'!$E$6:$E$24,"Ambos")+COUNTIFS('S4'!$B$6:$B$22,$A67,'S4'!$E$6:$E$22,"Diego")+COUNTIFS('S4'!$B$6:$B$22,$A67,'S4'!$E$6:$E$22,"Ambos")+COUNTIFS('S5'!$B$6:$B$20,$A67,'S5'!$E$6:$E$20,"Diego")+COUNTIFS('S5'!$B$6:$B$20,$A67,'S5'!$E$6:$E$20,"Ambos")+COUNTIFS('S6'!$B$6:$B$17,$A67,'S6'!$E$6:$E$17,"Diego")+COUNTIFS('S6'!$B$6:$B$17,$A67,'S6'!$E$6:$E$17,"Ambos")+COUNTIFS('S7'!$B$6:$B$19,$A67,'S7'!$E$6:$E$19,"Diego")+COUNTIFS('S7'!$B$6:$B$19,$A67,'S7'!$E$6:$E$19,"Ambos")+COUNTIFS('S8'!$B$6:$B$23,$A67,'S8'!$E$6:$E$23,"Diego")+COUNTIFS('S8'!$B$6:$B$23,$A67,'S8'!$E$6:$E$23,"Ambos")+COUNTIFS('S9'!$B$6:$B$15,$A67,'S9'!$E$6:$E$15,"Diego")+COUNTIFS('S9'!$B$6:$B$15,$A67,'S9'!$E$6:$E$15,"Ambos")+COUNTIFS('S10'!$B$6:$B$13,$A67,'S10'!$E$6:$E$13,"Diego")+COUNTIFS('S10'!$B$6:$B$13,$A67,'S10'!$E$6:$E$13,"Ambos")+COUNTIFS('Holgura'!$B$6:$B$11,$A67,'Holgura'!$E$6:$E$11,"Diego")+COUNTIFS('Holgura'!$B$6:$B$11,$A67,'Holgura'!$E$6:$E$11,"Ambos")+COUNTIFS('Entrega'!$B$6:$B$9,$A67,'Entrega'!$E$6:$E$9,"Diego")+COUNTIFS('Entrega'!$B$6:$B$9,$A67,'Entrega'!$E$6:$E$9,"Ambos")+COUNTIFS('Defensa'!$B$6:$B$10,$A67,'Defensa'!$E$6:$E$10,"Diego")+COUNTIFS('Defensa'!$B$6:$B$10,$A67,'Defensa'!$E$6:$E$10,"Ambos")</f>
         <v/>
       </c>
     </row>
@@ -10507,19 +10528,19 @@
         <v/>
       </c>
       <c r="D68" s="21">
-        <f>SUMIFS('S1'!$I$6:$I$32,'S1'!$B$6:$B$32,$A68,'S1'!$E$6:$E$32,"Víctor")+SUMIFS('S1'!$I$6:$I$32,'S1'!$B$6:$B$32,$A68,'S1'!$E$6:$E$32,"Ambos")+SUMIFS('S2'!$I$6:$I$23,'S2'!$B$6:$B$23,$A68,'S2'!$E$6:$E$23,"Víctor")+SUMIFS('S2'!$I$6:$I$23,'S2'!$B$6:$B$23,$A68,'S2'!$E$6:$E$23,"Ambos")+SUMIFS('S3'!$I$6:$I$19,'S3'!$B$6:$B$19,$A68,'S3'!$E$6:$E$19,"Víctor")+SUMIFS('S3'!$I$6:$I$19,'S3'!$B$6:$B$19,$A68,'S3'!$E$6:$E$19,"Ambos")+SUMIFS('S4'!$I$6:$I$20,'S4'!$B$6:$B$20,$A68,'S4'!$E$6:$E$20,"Víctor")+SUMIFS('S4'!$I$6:$I$20,'S4'!$B$6:$B$20,$A68,'S4'!$E$6:$E$20,"Ambos")+SUMIFS('S5'!$I$6:$I$20,'S5'!$B$6:$B$20,$A68,'S5'!$E$6:$E$20,"Víctor")+SUMIFS('S5'!$I$6:$I$20,'S5'!$B$6:$B$20,$A68,'S5'!$E$6:$E$20,"Ambos")+SUMIFS('S6'!$I$6:$I$17,'S6'!$B$6:$B$17,$A68,'S6'!$E$6:$E$17,"Víctor")+SUMIFS('S6'!$I$6:$I$17,'S6'!$B$6:$B$17,$A68,'S6'!$E$6:$E$17,"Ambos")+SUMIFS('S7'!$I$6:$I$19,'S7'!$B$6:$B$19,$A68,'S7'!$E$6:$E$19,"Víctor")+SUMIFS('S7'!$I$6:$I$19,'S7'!$B$6:$B$19,$A68,'S7'!$E$6:$E$19,"Ambos")+SUMIFS('S8'!$I$6:$I$23,'S8'!$B$6:$B$23,$A68,'S8'!$E$6:$E$23,"Víctor")+SUMIFS('S8'!$I$6:$I$23,'S8'!$B$6:$B$23,$A68,'S8'!$E$6:$E$23,"Ambos")+SUMIFS('S9'!$I$6:$I$15,'S9'!$B$6:$B$15,$A68,'S9'!$E$6:$E$15,"Víctor")+SUMIFS('S9'!$I$6:$I$15,'S9'!$B$6:$B$15,$A68,'S9'!$E$6:$E$15,"Ambos")+SUMIFS('S10'!$I$6:$I$13,'S10'!$B$6:$B$13,$A68,'S10'!$E$6:$E$13,"Víctor")+SUMIFS('S10'!$I$6:$I$13,'S10'!$B$6:$B$13,$A68,'S10'!$E$6:$E$13,"Ambos")+SUMIFS('Holgura'!$I$6:$I$11,'Holgura'!$B$6:$B$11,$A68,'Holgura'!$E$6:$E$11,"Víctor")+SUMIFS('Holgura'!$I$6:$I$11,'Holgura'!$B$6:$B$11,$A68,'Holgura'!$E$6:$E$11,"Ambos")+SUMIFS('Entrega'!$I$6:$I$9,'Entrega'!$B$6:$B$9,$A68,'Entrega'!$E$6:$E$9,"Víctor")+SUMIFS('Entrega'!$I$6:$I$9,'Entrega'!$B$6:$B$9,$A68,'Entrega'!$E$6:$E$9,"Ambos")+SUMIFS('Defensa'!$I$6:$I$10,'Defensa'!$B$6:$B$10,$A68,'Defensa'!$E$6:$E$10,"Víctor")+SUMIFS('Defensa'!$I$6:$I$10,'Defensa'!$B$6:$B$10,$A68,'Defensa'!$E$6:$E$10,"Ambos")</f>
+        <f>SUMIFS('S1'!$I$6:$I$32,'S1'!$B$6:$B$32,$A68,'S1'!$E$6:$E$32,"Víctor")+SUMIFS('S1'!$I$6:$I$32,'S1'!$B$6:$B$32,$A68,'S1'!$E$6:$E$32,"Ambos")+SUMIFS('S2'!$I$6:$I$23,'S2'!$B$6:$B$23,$A68,'S2'!$E$6:$E$23,"Víctor")+SUMIFS('S2'!$I$6:$I$23,'S2'!$B$6:$B$23,$A68,'S2'!$E$6:$E$23,"Ambos")+SUMIFS('S3'!$I$6:$I$24,'S3'!$B$6:$B$24,$A68,'S3'!$E$6:$E$24,"Víctor")+SUMIFS('S3'!$I$6:$I$24,'S3'!$B$6:$B$24,$A68,'S3'!$E$6:$E$24,"Ambos")+SUMIFS('S4'!$I$6:$I$22,'S4'!$B$6:$B$22,$A68,'S4'!$E$6:$E$22,"Víctor")+SUMIFS('S4'!$I$6:$I$22,'S4'!$B$6:$B$22,$A68,'S4'!$E$6:$E$22,"Ambos")+SUMIFS('S5'!$I$6:$I$20,'S5'!$B$6:$B$20,$A68,'S5'!$E$6:$E$20,"Víctor")+SUMIFS('S5'!$I$6:$I$20,'S5'!$B$6:$B$20,$A68,'S5'!$E$6:$E$20,"Ambos")+SUMIFS('S6'!$I$6:$I$17,'S6'!$B$6:$B$17,$A68,'S6'!$E$6:$E$17,"Víctor")+SUMIFS('S6'!$I$6:$I$17,'S6'!$B$6:$B$17,$A68,'S6'!$E$6:$E$17,"Ambos")+SUMIFS('S7'!$I$6:$I$19,'S7'!$B$6:$B$19,$A68,'S7'!$E$6:$E$19,"Víctor")+SUMIFS('S7'!$I$6:$I$19,'S7'!$B$6:$B$19,$A68,'S7'!$E$6:$E$19,"Ambos")+SUMIFS('S8'!$I$6:$I$23,'S8'!$B$6:$B$23,$A68,'S8'!$E$6:$E$23,"Víctor")+SUMIFS('S8'!$I$6:$I$23,'S8'!$B$6:$B$23,$A68,'S8'!$E$6:$E$23,"Ambos")+SUMIFS('S9'!$I$6:$I$15,'S9'!$B$6:$B$15,$A68,'S9'!$E$6:$E$15,"Víctor")+SUMIFS('S9'!$I$6:$I$15,'S9'!$B$6:$B$15,$A68,'S9'!$E$6:$E$15,"Ambos")+SUMIFS('S10'!$I$6:$I$13,'S10'!$B$6:$B$13,$A68,'S10'!$E$6:$E$13,"Víctor")+SUMIFS('S10'!$I$6:$I$13,'S10'!$B$6:$B$13,$A68,'S10'!$E$6:$E$13,"Ambos")+SUMIFS('Holgura'!$I$6:$I$11,'Holgura'!$B$6:$B$11,$A68,'Holgura'!$E$6:$E$11,"Víctor")+SUMIFS('Holgura'!$I$6:$I$11,'Holgura'!$B$6:$B$11,$A68,'Holgura'!$E$6:$E$11,"Ambos")+SUMIFS('Entrega'!$I$6:$I$9,'Entrega'!$B$6:$B$9,$A68,'Entrega'!$E$6:$E$9,"Víctor")+SUMIFS('Entrega'!$I$6:$I$9,'Entrega'!$B$6:$B$9,$A68,'Entrega'!$E$6:$E$9,"Ambos")+SUMIFS('Defensa'!$I$6:$I$10,'Defensa'!$B$6:$B$10,$A68,'Defensa'!$E$6:$E$10,"Víctor")+SUMIFS('Defensa'!$I$6:$I$10,'Defensa'!$B$6:$B$10,$A68,'Defensa'!$E$6:$E$10,"Ambos")</f>
         <v/>
       </c>
       <c r="E68" s="21">
-        <f>SUMIFS('S1'!$I$6:$I$32,'S1'!$B$6:$B$32,$A68,'S1'!$E$6:$E$32,"Diego")+SUMIFS('S1'!$I$6:$I$32,'S1'!$B$6:$B$32,$A68,'S1'!$E$6:$E$32,"Ambos")+SUMIFS('S2'!$I$6:$I$23,'S2'!$B$6:$B$23,$A68,'S2'!$E$6:$E$23,"Diego")+SUMIFS('S2'!$I$6:$I$23,'S2'!$B$6:$B$23,$A68,'S2'!$E$6:$E$23,"Ambos")+SUMIFS('S3'!$I$6:$I$19,'S3'!$B$6:$B$19,$A68,'S3'!$E$6:$E$19,"Diego")+SUMIFS('S3'!$I$6:$I$19,'S3'!$B$6:$B$19,$A68,'S3'!$E$6:$E$19,"Ambos")+SUMIFS('S4'!$I$6:$I$20,'S4'!$B$6:$B$20,$A68,'S4'!$E$6:$E$20,"Diego")+SUMIFS('S4'!$I$6:$I$20,'S4'!$B$6:$B$20,$A68,'S4'!$E$6:$E$20,"Ambos")+SUMIFS('S5'!$I$6:$I$20,'S5'!$B$6:$B$20,$A68,'S5'!$E$6:$E$20,"Diego")+SUMIFS('S5'!$I$6:$I$20,'S5'!$B$6:$B$20,$A68,'S5'!$E$6:$E$20,"Ambos")+SUMIFS('S6'!$I$6:$I$17,'S6'!$B$6:$B$17,$A68,'S6'!$E$6:$E$17,"Diego")+SUMIFS('S6'!$I$6:$I$17,'S6'!$B$6:$B$17,$A68,'S6'!$E$6:$E$17,"Ambos")+SUMIFS('S7'!$I$6:$I$19,'S7'!$B$6:$B$19,$A68,'S7'!$E$6:$E$19,"Diego")+SUMIFS('S7'!$I$6:$I$19,'S7'!$B$6:$B$19,$A68,'S7'!$E$6:$E$19,"Ambos")+SUMIFS('S8'!$I$6:$I$23,'S8'!$B$6:$B$23,$A68,'S8'!$E$6:$E$23,"Diego")+SUMIFS('S8'!$I$6:$I$23,'S8'!$B$6:$B$23,$A68,'S8'!$E$6:$E$23,"Ambos")+SUMIFS('S9'!$I$6:$I$15,'S9'!$B$6:$B$15,$A68,'S9'!$E$6:$E$15,"Diego")+SUMIFS('S9'!$I$6:$I$15,'S9'!$B$6:$B$15,$A68,'S9'!$E$6:$E$15,"Ambos")+SUMIFS('S10'!$I$6:$I$13,'S10'!$B$6:$B$13,$A68,'S10'!$E$6:$E$13,"Diego")+SUMIFS('S10'!$I$6:$I$13,'S10'!$B$6:$B$13,$A68,'S10'!$E$6:$E$13,"Ambos")+SUMIFS('Holgura'!$I$6:$I$11,'Holgura'!$B$6:$B$11,$A68,'Holgura'!$E$6:$E$11,"Diego")+SUMIFS('Holgura'!$I$6:$I$11,'Holgura'!$B$6:$B$11,$A68,'Holgura'!$E$6:$E$11,"Ambos")+SUMIFS('Entrega'!$I$6:$I$9,'Entrega'!$B$6:$B$9,$A68,'Entrega'!$E$6:$E$9,"Diego")+SUMIFS('Entrega'!$I$6:$I$9,'Entrega'!$B$6:$B$9,$A68,'Entrega'!$E$6:$E$9,"Ambos")+SUMIFS('Defensa'!$I$6:$I$10,'Defensa'!$B$6:$B$10,$A68,'Defensa'!$E$6:$E$10,"Diego")+SUMIFS('Defensa'!$I$6:$I$10,'Defensa'!$B$6:$B$10,$A68,'Defensa'!$E$6:$E$10,"Ambos")</f>
+        <f>SUMIFS('S1'!$I$6:$I$32,'S1'!$B$6:$B$32,$A68,'S1'!$E$6:$E$32,"Diego")+SUMIFS('S1'!$I$6:$I$32,'S1'!$B$6:$B$32,$A68,'S1'!$E$6:$E$32,"Ambos")+SUMIFS('S2'!$I$6:$I$23,'S2'!$B$6:$B$23,$A68,'S2'!$E$6:$E$23,"Diego")+SUMIFS('S2'!$I$6:$I$23,'S2'!$B$6:$B$23,$A68,'S2'!$E$6:$E$23,"Ambos")+SUMIFS('S3'!$I$6:$I$24,'S3'!$B$6:$B$24,$A68,'S3'!$E$6:$E$24,"Diego")+SUMIFS('S3'!$I$6:$I$24,'S3'!$B$6:$B$24,$A68,'S3'!$E$6:$E$24,"Ambos")+SUMIFS('S4'!$I$6:$I$22,'S4'!$B$6:$B$22,$A68,'S4'!$E$6:$E$22,"Diego")+SUMIFS('S4'!$I$6:$I$22,'S4'!$B$6:$B$22,$A68,'S4'!$E$6:$E$22,"Ambos")+SUMIFS('S5'!$I$6:$I$20,'S5'!$B$6:$B$20,$A68,'S5'!$E$6:$E$20,"Diego")+SUMIFS('S5'!$I$6:$I$20,'S5'!$B$6:$B$20,$A68,'S5'!$E$6:$E$20,"Ambos")+SUMIFS('S6'!$I$6:$I$17,'S6'!$B$6:$B$17,$A68,'S6'!$E$6:$E$17,"Diego")+SUMIFS('S6'!$I$6:$I$17,'S6'!$B$6:$B$17,$A68,'S6'!$E$6:$E$17,"Ambos")+SUMIFS('S7'!$I$6:$I$19,'S7'!$B$6:$B$19,$A68,'S7'!$E$6:$E$19,"Diego")+SUMIFS('S7'!$I$6:$I$19,'S7'!$B$6:$B$19,$A68,'S7'!$E$6:$E$19,"Ambos")+SUMIFS('S8'!$I$6:$I$23,'S8'!$B$6:$B$23,$A68,'S8'!$E$6:$E$23,"Diego")+SUMIFS('S8'!$I$6:$I$23,'S8'!$B$6:$B$23,$A68,'S8'!$E$6:$E$23,"Ambos")+SUMIFS('S9'!$I$6:$I$15,'S9'!$B$6:$B$15,$A68,'S9'!$E$6:$E$15,"Diego")+SUMIFS('S9'!$I$6:$I$15,'S9'!$B$6:$B$15,$A68,'S9'!$E$6:$E$15,"Ambos")+SUMIFS('S10'!$I$6:$I$13,'S10'!$B$6:$B$13,$A68,'S10'!$E$6:$E$13,"Diego")+SUMIFS('S10'!$I$6:$I$13,'S10'!$B$6:$B$13,$A68,'S10'!$E$6:$E$13,"Ambos")+SUMIFS('Holgura'!$I$6:$I$11,'Holgura'!$B$6:$B$11,$A68,'Holgura'!$E$6:$E$11,"Diego")+SUMIFS('Holgura'!$I$6:$I$11,'Holgura'!$B$6:$B$11,$A68,'Holgura'!$E$6:$E$11,"Ambos")+SUMIFS('Entrega'!$I$6:$I$9,'Entrega'!$B$6:$B$9,$A68,'Entrega'!$E$6:$E$9,"Diego")+SUMIFS('Entrega'!$I$6:$I$9,'Entrega'!$B$6:$B$9,$A68,'Entrega'!$E$6:$E$9,"Ambos")+SUMIFS('Defensa'!$I$6:$I$10,'Defensa'!$B$6:$B$10,$A68,'Defensa'!$E$6:$E$10,"Diego")+SUMIFS('Defensa'!$I$6:$I$10,'Defensa'!$B$6:$B$10,$A68,'Defensa'!$E$6:$E$10,"Ambos")</f>
         <v/>
       </c>
       <c r="F68" s="21">
-        <f>COUNTIFS('S1'!$B$6:$B$32,$A68,'S1'!$E$6:$E$32,"Víctor")+COUNTIFS('S1'!$B$6:$B$32,$A68,'S1'!$E$6:$E$32,"Ambos")+COUNTIFS('S2'!$B$6:$B$23,$A68,'S2'!$E$6:$E$23,"Víctor")+COUNTIFS('S2'!$B$6:$B$23,$A68,'S2'!$E$6:$E$23,"Ambos")+COUNTIFS('S3'!$B$6:$B$19,$A68,'S3'!$E$6:$E$19,"Víctor")+COUNTIFS('S3'!$B$6:$B$19,$A68,'S3'!$E$6:$E$19,"Ambos")+COUNTIFS('S4'!$B$6:$B$20,$A68,'S4'!$E$6:$E$20,"Víctor")+COUNTIFS('S4'!$B$6:$B$20,$A68,'S4'!$E$6:$E$20,"Ambos")+COUNTIFS('S5'!$B$6:$B$20,$A68,'S5'!$E$6:$E$20,"Víctor")+COUNTIFS('S5'!$B$6:$B$20,$A68,'S5'!$E$6:$E$20,"Ambos")+COUNTIFS('S6'!$B$6:$B$17,$A68,'S6'!$E$6:$E$17,"Víctor")+COUNTIFS('S6'!$B$6:$B$17,$A68,'S6'!$E$6:$E$17,"Ambos")+COUNTIFS('S7'!$B$6:$B$19,$A68,'S7'!$E$6:$E$19,"Víctor")+COUNTIFS('S7'!$B$6:$B$19,$A68,'S7'!$E$6:$E$19,"Ambos")+COUNTIFS('S8'!$B$6:$B$23,$A68,'S8'!$E$6:$E$23,"Víctor")+COUNTIFS('S8'!$B$6:$B$23,$A68,'S8'!$E$6:$E$23,"Ambos")+COUNTIFS('S9'!$B$6:$B$15,$A68,'S9'!$E$6:$E$15,"Víctor")+COUNTIFS('S9'!$B$6:$B$15,$A68,'S9'!$E$6:$E$15,"Ambos")+COUNTIFS('S10'!$B$6:$B$13,$A68,'S10'!$E$6:$E$13,"Víctor")+COUNTIFS('S10'!$B$6:$B$13,$A68,'S10'!$E$6:$E$13,"Ambos")+COUNTIFS('Holgura'!$B$6:$B$11,$A68,'Holgura'!$E$6:$E$11,"Víctor")+COUNTIFS('Holgura'!$B$6:$B$11,$A68,'Holgura'!$E$6:$E$11,"Ambos")+COUNTIFS('Entrega'!$B$6:$B$9,$A68,'Entrega'!$E$6:$E$9,"Víctor")+COUNTIFS('Entrega'!$B$6:$B$9,$A68,'Entrega'!$E$6:$E$9,"Ambos")+COUNTIFS('Defensa'!$B$6:$B$10,$A68,'Defensa'!$E$6:$E$10,"Víctor")+COUNTIFS('Defensa'!$B$6:$B$10,$A68,'Defensa'!$E$6:$E$10,"Ambos")</f>
+        <f>COUNTIFS('S1'!$B$6:$B$32,$A68,'S1'!$E$6:$E$32,"Víctor")+COUNTIFS('S1'!$B$6:$B$32,$A68,'S1'!$E$6:$E$32,"Ambos")+COUNTIFS('S2'!$B$6:$B$23,$A68,'S2'!$E$6:$E$23,"Víctor")+COUNTIFS('S2'!$B$6:$B$23,$A68,'S2'!$E$6:$E$23,"Ambos")+COUNTIFS('S3'!$B$6:$B$24,$A68,'S3'!$E$6:$E$24,"Víctor")+COUNTIFS('S3'!$B$6:$B$24,$A68,'S3'!$E$6:$E$24,"Ambos")+COUNTIFS('S4'!$B$6:$B$22,$A68,'S4'!$E$6:$E$22,"Víctor")+COUNTIFS('S4'!$B$6:$B$22,$A68,'S4'!$E$6:$E$22,"Ambos")+COUNTIFS('S5'!$B$6:$B$20,$A68,'S5'!$E$6:$E$20,"Víctor")+COUNTIFS('S5'!$B$6:$B$20,$A68,'S5'!$E$6:$E$20,"Ambos")+COUNTIFS('S6'!$B$6:$B$17,$A68,'S6'!$E$6:$E$17,"Víctor")+COUNTIFS('S6'!$B$6:$B$17,$A68,'S6'!$E$6:$E$17,"Ambos")+COUNTIFS('S7'!$B$6:$B$19,$A68,'S7'!$E$6:$E$19,"Víctor")+COUNTIFS('S7'!$B$6:$B$19,$A68,'S7'!$E$6:$E$19,"Ambos")+COUNTIFS('S8'!$B$6:$B$23,$A68,'S8'!$E$6:$E$23,"Víctor")+COUNTIFS('S8'!$B$6:$B$23,$A68,'S8'!$E$6:$E$23,"Ambos")+COUNTIFS('S9'!$B$6:$B$15,$A68,'S9'!$E$6:$E$15,"Víctor")+COUNTIFS('S9'!$B$6:$B$15,$A68,'S9'!$E$6:$E$15,"Ambos")+COUNTIFS('S10'!$B$6:$B$13,$A68,'S10'!$E$6:$E$13,"Víctor")+COUNTIFS('S10'!$B$6:$B$13,$A68,'S10'!$E$6:$E$13,"Ambos")+COUNTIFS('Holgura'!$B$6:$B$11,$A68,'Holgura'!$E$6:$E$11,"Víctor")+COUNTIFS('Holgura'!$B$6:$B$11,$A68,'Holgura'!$E$6:$E$11,"Ambos")+COUNTIFS('Entrega'!$B$6:$B$9,$A68,'Entrega'!$E$6:$E$9,"Víctor")+COUNTIFS('Entrega'!$B$6:$B$9,$A68,'Entrega'!$E$6:$E$9,"Ambos")+COUNTIFS('Defensa'!$B$6:$B$10,$A68,'Defensa'!$E$6:$E$10,"Víctor")+COUNTIFS('Defensa'!$B$6:$B$10,$A68,'Defensa'!$E$6:$E$10,"Ambos")</f>
         <v/>
       </c>
       <c r="G68" s="21">
-        <f>COUNTIFS('S1'!$B$6:$B$32,$A68,'S1'!$E$6:$E$32,"Diego")+COUNTIFS('S1'!$B$6:$B$32,$A68,'S1'!$E$6:$E$32,"Ambos")+COUNTIFS('S2'!$B$6:$B$23,$A68,'S2'!$E$6:$E$23,"Diego")+COUNTIFS('S2'!$B$6:$B$23,$A68,'S2'!$E$6:$E$23,"Ambos")+COUNTIFS('S3'!$B$6:$B$19,$A68,'S3'!$E$6:$E$19,"Diego")+COUNTIFS('S3'!$B$6:$B$19,$A68,'S3'!$E$6:$E$19,"Ambos")+COUNTIFS('S4'!$B$6:$B$20,$A68,'S4'!$E$6:$E$20,"Diego")+COUNTIFS('S4'!$B$6:$B$20,$A68,'S4'!$E$6:$E$20,"Ambos")+COUNTIFS('S5'!$B$6:$B$20,$A68,'S5'!$E$6:$E$20,"Diego")+COUNTIFS('S5'!$B$6:$B$20,$A68,'S5'!$E$6:$E$20,"Ambos")+COUNTIFS('S6'!$B$6:$B$17,$A68,'S6'!$E$6:$E$17,"Diego")+COUNTIFS('S6'!$B$6:$B$17,$A68,'S6'!$E$6:$E$17,"Ambos")+COUNTIFS('S7'!$B$6:$B$19,$A68,'S7'!$E$6:$E$19,"Diego")+COUNTIFS('S7'!$B$6:$B$19,$A68,'S7'!$E$6:$E$19,"Ambos")+COUNTIFS('S8'!$B$6:$B$23,$A68,'S8'!$E$6:$E$23,"Diego")+COUNTIFS('S8'!$B$6:$B$23,$A68,'S8'!$E$6:$E$23,"Ambos")+COUNTIFS('S9'!$B$6:$B$15,$A68,'S9'!$E$6:$E$15,"Diego")+COUNTIFS('S9'!$B$6:$B$15,$A68,'S9'!$E$6:$E$15,"Ambos")+COUNTIFS('S10'!$B$6:$B$13,$A68,'S10'!$E$6:$E$13,"Diego")+COUNTIFS('S10'!$B$6:$B$13,$A68,'S10'!$E$6:$E$13,"Ambos")+COUNTIFS('Holgura'!$B$6:$B$11,$A68,'Holgura'!$E$6:$E$11,"Diego")+COUNTIFS('Holgura'!$B$6:$B$11,$A68,'Holgura'!$E$6:$E$11,"Ambos")+COUNTIFS('Entrega'!$B$6:$B$9,$A68,'Entrega'!$E$6:$E$9,"Diego")+COUNTIFS('Entrega'!$B$6:$B$9,$A68,'Entrega'!$E$6:$E$9,"Ambos")+COUNTIFS('Defensa'!$B$6:$B$10,$A68,'Defensa'!$E$6:$E$10,"Diego")+COUNTIFS('Defensa'!$B$6:$B$10,$A68,'Defensa'!$E$6:$E$10,"Ambos")</f>
+        <f>COUNTIFS('S1'!$B$6:$B$32,$A68,'S1'!$E$6:$E$32,"Diego")+COUNTIFS('S1'!$B$6:$B$32,$A68,'S1'!$E$6:$E$32,"Ambos")+COUNTIFS('S2'!$B$6:$B$23,$A68,'S2'!$E$6:$E$23,"Diego")+COUNTIFS('S2'!$B$6:$B$23,$A68,'S2'!$E$6:$E$23,"Ambos")+COUNTIFS('S3'!$B$6:$B$24,$A68,'S3'!$E$6:$E$24,"Diego")+COUNTIFS('S3'!$B$6:$B$24,$A68,'S3'!$E$6:$E$24,"Ambos")+COUNTIFS('S4'!$B$6:$B$22,$A68,'S4'!$E$6:$E$22,"Diego")+COUNTIFS('S4'!$B$6:$B$22,$A68,'S4'!$E$6:$E$22,"Ambos")+COUNTIFS('S5'!$B$6:$B$20,$A68,'S5'!$E$6:$E$20,"Diego")+COUNTIFS('S5'!$B$6:$B$20,$A68,'S5'!$E$6:$E$20,"Ambos")+COUNTIFS('S6'!$B$6:$B$17,$A68,'S6'!$E$6:$E$17,"Diego")+COUNTIFS('S6'!$B$6:$B$17,$A68,'S6'!$E$6:$E$17,"Ambos")+COUNTIFS('S7'!$B$6:$B$19,$A68,'S7'!$E$6:$E$19,"Diego")+COUNTIFS('S7'!$B$6:$B$19,$A68,'S7'!$E$6:$E$19,"Ambos")+COUNTIFS('S8'!$B$6:$B$23,$A68,'S8'!$E$6:$E$23,"Diego")+COUNTIFS('S8'!$B$6:$B$23,$A68,'S8'!$E$6:$E$23,"Ambos")+COUNTIFS('S9'!$B$6:$B$15,$A68,'S9'!$E$6:$E$15,"Diego")+COUNTIFS('S9'!$B$6:$B$15,$A68,'S9'!$E$6:$E$15,"Ambos")+COUNTIFS('S10'!$B$6:$B$13,$A68,'S10'!$E$6:$E$13,"Diego")+COUNTIFS('S10'!$B$6:$B$13,$A68,'S10'!$E$6:$E$13,"Ambos")+COUNTIFS('Holgura'!$B$6:$B$11,$A68,'Holgura'!$E$6:$E$11,"Diego")+COUNTIFS('Holgura'!$B$6:$B$11,$A68,'Holgura'!$E$6:$E$11,"Ambos")+COUNTIFS('Entrega'!$B$6:$B$9,$A68,'Entrega'!$E$6:$E$9,"Diego")+COUNTIFS('Entrega'!$B$6:$B$9,$A68,'Entrega'!$E$6:$E$9,"Ambos")+COUNTIFS('Defensa'!$B$6:$B$10,$A68,'Defensa'!$E$6:$E$10,"Diego")+COUNTIFS('Defensa'!$B$6:$B$10,$A68,'Defensa'!$E$6:$E$10,"Ambos")</f>
         <v/>
       </c>
     </row>
@@ -10536,19 +10557,19 @@
         <v/>
       </c>
       <c r="D69" s="21">
-        <f>SUMIFS('S1'!$I$6:$I$32,'S1'!$B$6:$B$32,$A69,'S1'!$E$6:$E$32,"Víctor")+SUMIFS('S1'!$I$6:$I$32,'S1'!$B$6:$B$32,$A69,'S1'!$E$6:$E$32,"Ambos")+SUMIFS('S2'!$I$6:$I$23,'S2'!$B$6:$B$23,$A69,'S2'!$E$6:$E$23,"Víctor")+SUMIFS('S2'!$I$6:$I$23,'S2'!$B$6:$B$23,$A69,'S2'!$E$6:$E$23,"Ambos")+SUMIFS('S3'!$I$6:$I$19,'S3'!$B$6:$B$19,$A69,'S3'!$E$6:$E$19,"Víctor")+SUMIFS('S3'!$I$6:$I$19,'S3'!$B$6:$B$19,$A69,'S3'!$E$6:$E$19,"Ambos")+SUMIFS('S4'!$I$6:$I$20,'S4'!$B$6:$B$20,$A69,'S4'!$E$6:$E$20,"Víctor")+SUMIFS('S4'!$I$6:$I$20,'S4'!$B$6:$B$20,$A69,'S4'!$E$6:$E$20,"Ambos")+SUMIFS('S5'!$I$6:$I$20,'S5'!$B$6:$B$20,$A69,'S5'!$E$6:$E$20,"Víctor")+SUMIFS('S5'!$I$6:$I$20,'S5'!$B$6:$B$20,$A69,'S5'!$E$6:$E$20,"Ambos")+SUMIFS('S6'!$I$6:$I$17,'S6'!$B$6:$B$17,$A69,'S6'!$E$6:$E$17,"Víctor")+SUMIFS('S6'!$I$6:$I$17,'S6'!$B$6:$B$17,$A69,'S6'!$E$6:$E$17,"Ambos")+SUMIFS('S7'!$I$6:$I$19,'S7'!$B$6:$B$19,$A69,'S7'!$E$6:$E$19,"Víctor")+SUMIFS('S7'!$I$6:$I$19,'S7'!$B$6:$B$19,$A69,'S7'!$E$6:$E$19,"Ambos")+SUMIFS('S8'!$I$6:$I$23,'S8'!$B$6:$B$23,$A69,'S8'!$E$6:$E$23,"Víctor")+SUMIFS('S8'!$I$6:$I$23,'S8'!$B$6:$B$23,$A69,'S8'!$E$6:$E$23,"Ambos")+SUMIFS('S9'!$I$6:$I$15,'S9'!$B$6:$B$15,$A69,'S9'!$E$6:$E$15,"Víctor")+SUMIFS('S9'!$I$6:$I$15,'S9'!$B$6:$B$15,$A69,'S9'!$E$6:$E$15,"Ambos")+SUMIFS('S10'!$I$6:$I$13,'S10'!$B$6:$B$13,$A69,'S10'!$E$6:$E$13,"Víctor")+SUMIFS('S10'!$I$6:$I$13,'S10'!$B$6:$B$13,$A69,'S10'!$E$6:$E$13,"Ambos")+SUMIFS('Holgura'!$I$6:$I$11,'Holgura'!$B$6:$B$11,$A69,'Holgura'!$E$6:$E$11,"Víctor")+SUMIFS('Holgura'!$I$6:$I$11,'Holgura'!$B$6:$B$11,$A69,'Holgura'!$E$6:$E$11,"Ambos")+SUMIFS('Entrega'!$I$6:$I$9,'Entrega'!$B$6:$B$9,$A69,'Entrega'!$E$6:$E$9,"Víctor")+SUMIFS('Entrega'!$I$6:$I$9,'Entrega'!$B$6:$B$9,$A69,'Entrega'!$E$6:$E$9,"Ambos")+SUMIFS('Defensa'!$I$6:$I$10,'Defensa'!$B$6:$B$10,$A69,'Defensa'!$E$6:$E$10,"Víctor")+SUMIFS('Defensa'!$I$6:$I$10,'Defensa'!$B$6:$B$10,$A69,'Defensa'!$E$6:$E$10,"Ambos")</f>
+        <f>SUMIFS('S1'!$I$6:$I$32,'S1'!$B$6:$B$32,$A69,'S1'!$E$6:$E$32,"Víctor")+SUMIFS('S1'!$I$6:$I$32,'S1'!$B$6:$B$32,$A69,'S1'!$E$6:$E$32,"Ambos")+SUMIFS('S2'!$I$6:$I$23,'S2'!$B$6:$B$23,$A69,'S2'!$E$6:$E$23,"Víctor")+SUMIFS('S2'!$I$6:$I$23,'S2'!$B$6:$B$23,$A69,'S2'!$E$6:$E$23,"Ambos")+SUMIFS('S3'!$I$6:$I$24,'S3'!$B$6:$B$24,$A69,'S3'!$E$6:$E$24,"Víctor")+SUMIFS('S3'!$I$6:$I$24,'S3'!$B$6:$B$24,$A69,'S3'!$E$6:$E$24,"Ambos")+SUMIFS('S4'!$I$6:$I$22,'S4'!$B$6:$B$22,$A69,'S4'!$E$6:$E$22,"Víctor")+SUMIFS('S4'!$I$6:$I$22,'S4'!$B$6:$B$22,$A69,'S4'!$E$6:$E$22,"Ambos")+SUMIFS('S5'!$I$6:$I$20,'S5'!$B$6:$B$20,$A69,'S5'!$E$6:$E$20,"Víctor")+SUMIFS('S5'!$I$6:$I$20,'S5'!$B$6:$B$20,$A69,'S5'!$E$6:$E$20,"Ambos")+SUMIFS('S6'!$I$6:$I$17,'S6'!$B$6:$B$17,$A69,'S6'!$E$6:$E$17,"Víctor")+SUMIFS('S6'!$I$6:$I$17,'S6'!$B$6:$B$17,$A69,'S6'!$E$6:$E$17,"Ambos")+SUMIFS('S7'!$I$6:$I$19,'S7'!$B$6:$B$19,$A69,'S7'!$E$6:$E$19,"Víctor")+SUMIFS('S7'!$I$6:$I$19,'S7'!$B$6:$B$19,$A69,'S7'!$E$6:$E$19,"Ambos")+SUMIFS('S8'!$I$6:$I$23,'S8'!$B$6:$B$23,$A69,'S8'!$E$6:$E$23,"Víctor")+SUMIFS('S8'!$I$6:$I$23,'S8'!$B$6:$B$23,$A69,'S8'!$E$6:$E$23,"Ambos")+SUMIFS('S9'!$I$6:$I$15,'S9'!$B$6:$B$15,$A69,'S9'!$E$6:$E$15,"Víctor")+SUMIFS('S9'!$I$6:$I$15,'S9'!$B$6:$B$15,$A69,'S9'!$E$6:$E$15,"Ambos")+SUMIFS('S10'!$I$6:$I$13,'S10'!$B$6:$B$13,$A69,'S10'!$E$6:$E$13,"Víctor")+SUMIFS('S10'!$I$6:$I$13,'S10'!$B$6:$B$13,$A69,'S10'!$E$6:$E$13,"Ambos")+SUMIFS('Holgura'!$I$6:$I$11,'Holgura'!$B$6:$B$11,$A69,'Holgura'!$E$6:$E$11,"Víctor")+SUMIFS('Holgura'!$I$6:$I$11,'Holgura'!$B$6:$B$11,$A69,'Holgura'!$E$6:$E$11,"Ambos")+SUMIFS('Entrega'!$I$6:$I$9,'Entrega'!$B$6:$B$9,$A69,'Entrega'!$E$6:$E$9,"Víctor")+SUMIFS('Entrega'!$I$6:$I$9,'Entrega'!$B$6:$B$9,$A69,'Entrega'!$E$6:$E$9,"Ambos")+SUMIFS('Defensa'!$I$6:$I$10,'Defensa'!$B$6:$B$10,$A69,'Defensa'!$E$6:$E$10,"Víctor")+SUMIFS('Defensa'!$I$6:$I$10,'Defensa'!$B$6:$B$10,$A69,'Defensa'!$E$6:$E$10,"Ambos")</f>
         <v/>
       </c>
       <c r="E69" s="21">
-        <f>SUMIFS('S1'!$I$6:$I$32,'S1'!$B$6:$B$32,$A69,'S1'!$E$6:$E$32,"Diego")+SUMIFS('S1'!$I$6:$I$32,'S1'!$B$6:$B$32,$A69,'S1'!$E$6:$E$32,"Ambos")+SUMIFS('S2'!$I$6:$I$23,'S2'!$B$6:$B$23,$A69,'S2'!$E$6:$E$23,"Diego")+SUMIFS('S2'!$I$6:$I$23,'S2'!$B$6:$B$23,$A69,'S2'!$E$6:$E$23,"Ambos")+SUMIFS('S3'!$I$6:$I$19,'S3'!$B$6:$B$19,$A69,'S3'!$E$6:$E$19,"Diego")+SUMIFS('S3'!$I$6:$I$19,'S3'!$B$6:$B$19,$A69,'S3'!$E$6:$E$19,"Ambos")+SUMIFS('S4'!$I$6:$I$20,'S4'!$B$6:$B$20,$A69,'S4'!$E$6:$E$20,"Diego")+SUMIFS('S4'!$I$6:$I$20,'S4'!$B$6:$B$20,$A69,'S4'!$E$6:$E$20,"Ambos")+SUMIFS('S5'!$I$6:$I$20,'S5'!$B$6:$B$20,$A69,'S5'!$E$6:$E$20,"Diego")+SUMIFS('S5'!$I$6:$I$20,'S5'!$B$6:$B$20,$A69,'S5'!$E$6:$E$20,"Ambos")+SUMIFS('S6'!$I$6:$I$17,'S6'!$B$6:$B$17,$A69,'S6'!$E$6:$E$17,"Diego")+SUMIFS('S6'!$I$6:$I$17,'S6'!$B$6:$B$17,$A69,'S6'!$E$6:$E$17,"Ambos")+SUMIFS('S7'!$I$6:$I$19,'S7'!$B$6:$B$19,$A69,'S7'!$E$6:$E$19,"Diego")+SUMIFS('S7'!$I$6:$I$19,'S7'!$B$6:$B$19,$A69,'S7'!$E$6:$E$19,"Ambos")+SUMIFS('S8'!$I$6:$I$23,'S8'!$B$6:$B$23,$A69,'S8'!$E$6:$E$23,"Diego")+SUMIFS('S8'!$I$6:$I$23,'S8'!$B$6:$B$23,$A69,'S8'!$E$6:$E$23,"Ambos")+SUMIFS('S9'!$I$6:$I$15,'S9'!$B$6:$B$15,$A69,'S9'!$E$6:$E$15,"Diego")+SUMIFS('S9'!$I$6:$I$15,'S9'!$B$6:$B$15,$A69,'S9'!$E$6:$E$15,"Ambos")+SUMIFS('S10'!$I$6:$I$13,'S10'!$B$6:$B$13,$A69,'S10'!$E$6:$E$13,"Diego")+SUMIFS('S10'!$I$6:$I$13,'S10'!$B$6:$B$13,$A69,'S10'!$E$6:$E$13,"Ambos")+SUMIFS('Holgura'!$I$6:$I$11,'Holgura'!$B$6:$B$11,$A69,'Holgura'!$E$6:$E$11,"Diego")+SUMIFS('Holgura'!$I$6:$I$11,'Holgura'!$B$6:$B$11,$A69,'Holgura'!$E$6:$E$11,"Ambos")+SUMIFS('Entrega'!$I$6:$I$9,'Entrega'!$B$6:$B$9,$A69,'Entrega'!$E$6:$E$9,"Diego")+SUMIFS('Entrega'!$I$6:$I$9,'Entrega'!$B$6:$B$9,$A69,'Entrega'!$E$6:$E$9,"Ambos")+SUMIFS('Defensa'!$I$6:$I$10,'Defensa'!$B$6:$B$10,$A69,'Defensa'!$E$6:$E$10,"Diego")+SUMIFS('Defensa'!$I$6:$I$10,'Defensa'!$B$6:$B$10,$A69,'Defensa'!$E$6:$E$10,"Ambos")</f>
+        <f>SUMIFS('S1'!$I$6:$I$32,'S1'!$B$6:$B$32,$A69,'S1'!$E$6:$E$32,"Diego")+SUMIFS('S1'!$I$6:$I$32,'S1'!$B$6:$B$32,$A69,'S1'!$E$6:$E$32,"Ambos")+SUMIFS('S2'!$I$6:$I$23,'S2'!$B$6:$B$23,$A69,'S2'!$E$6:$E$23,"Diego")+SUMIFS('S2'!$I$6:$I$23,'S2'!$B$6:$B$23,$A69,'S2'!$E$6:$E$23,"Ambos")+SUMIFS('S3'!$I$6:$I$24,'S3'!$B$6:$B$24,$A69,'S3'!$E$6:$E$24,"Diego")+SUMIFS('S3'!$I$6:$I$24,'S3'!$B$6:$B$24,$A69,'S3'!$E$6:$E$24,"Ambos")+SUMIFS('S4'!$I$6:$I$22,'S4'!$B$6:$B$22,$A69,'S4'!$E$6:$E$22,"Diego")+SUMIFS('S4'!$I$6:$I$22,'S4'!$B$6:$B$22,$A69,'S4'!$E$6:$E$22,"Ambos")+SUMIFS('S5'!$I$6:$I$20,'S5'!$B$6:$B$20,$A69,'S5'!$E$6:$E$20,"Diego")+SUMIFS('S5'!$I$6:$I$20,'S5'!$B$6:$B$20,$A69,'S5'!$E$6:$E$20,"Ambos")+SUMIFS('S6'!$I$6:$I$17,'S6'!$B$6:$B$17,$A69,'S6'!$E$6:$E$17,"Diego")+SUMIFS('S6'!$I$6:$I$17,'S6'!$B$6:$B$17,$A69,'S6'!$E$6:$E$17,"Ambos")+SUMIFS('S7'!$I$6:$I$19,'S7'!$B$6:$B$19,$A69,'S7'!$E$6:$E$19,"Diego")+SUMIFS('S7'!$I$6:$I$19,'S7'!$B$6:$B$19,$A69,'S7'!$E$6:$E$19,"Ambos")+SUMIFS('S8'!$I$6:$I$23,'S8'!$B$6:$B$23,$A69,'S8'!$E$6:$E$23,"Diego")+SUMIFS('S8'!$I$6:$I$23,'S8'!$B$6:$B$23,$A69,'S8'!$E$6:$E$23,"Ambos")+SUMIFS('S9'!$I$6:$I$15,'S9'!$B$6:$B$15,$A69,'S9'!$E$6:$E$15,"Diego")+SUMIFS('S9'!$I$6:$I$15,'S9'!$B$6:$B$15,$A69,'S9'!$E$6:$E$15,"Ambos")+SUMIFS('S10'!$I$6:$I$13,'S10'!$B$6:$B$13,$A69,'S10'!$E$6:$E$13,"Diego")+SUMIFS('S10'!$I$6:$I$13,'S10'!$B$6:$B$13,$A69,'S10'!$E$6:$E$13,"Ambos")+SUMIFS('Holgura'!$I$6:$I$11,'Holgura'!$B$6:$B$11,$A69,'Holgura'!$E$6:$E$11,"Diego")+SUMIFS('Holgura'!$I$6:$I$11,'Holgura'!$B$6:$B$11,$A69,'Holgura'!$E$6:$E$11,"Ambos")+SUMIFS('Entrega'!$I$6:$I$9,'Entrega'!$B$6:$B$9,$A69,'Entrega'!$E$6:$E$9,"Diego")+SUMIFS('Entrega'!$I$6:$I$9,'Entrega'!$B$6:$B$9,$A69,'Entrega'!$E$6:$E$9,"Ambos")+SUMIFS('Defensa'!$I$6:$I$10,'Defensa'!$B$6:$B$10,$A69,'Defensa'!$E$6:$E$10,"Diego")+SUMIFS('Defensa'!$I$6:$I$10,'Defensa'!$B$6:$B$10,$A69,'Defensa'!$E$6:$E$10,"Ambos")</f>
         <v/>
       </c>
       <c r="F69" s="21">
-        <f>COUNTIFS('S1'!$B$6:$B$32,$A69,'S1'!$E$6:$E$32,"Víctor")+COUNTIFS('S1'!$B$6:$B$32,$A69,'S1'!$E$6:$E$32,"Ambos")+COUNTIFS('S2'!$B$6:$B$23,$A69,'S2'!$E$6:$E$23,"Víctor")+COUNTIFS('S2'!$B$6:$B$23,$A69,'S2'!$E$6:$E$23,"Ambos")+COUNTIFS('S3'!$B$6:$B$19,$A69,'S3'!$E$6:$E$19,"Víctor")+COUNTIFS('S3'!$B$6:$B$19,$A69,'S3'!$E$6:$E$19,"Ambos")+COUNTIFS('S4'!$B$6:$B$20,$A69,'S4'!$E$6:$E$20,"Víctor")+COUNTIFS('S4'!$B$6:$B$20,$A69,'S4'!$E$6:$E$20,"Ambos")+COUNTIFS('S5'!$B$6:$B$20,$A69,'S5'!$E$6:$E$20,"Víctor")+COUNTIFS('S5'!$B$6:$B$20,$A69,'S5'!$E$6:$E$20,"Ambos")+COUNTIFS('S6'!$B$6:$B$17,$A69,'S6'!$E$6:$E$17,"Víctor")+COUNTIFS('S6'!$B$6:$B$17,$A69,'S6'!$E$6:$E$17,"Ambos")+COUNTIFS('S7'!$B$6:$B$19,$A69,'S7'!$E$6:$E$19,"Víctor")+COUNTIFS('S7'!$B$6:$B$19,$A69,'S7'!$E$6:$E$19,"Ambos")+COUNTIFS('S8'!$B$6:$B$23,$A69,'S8'!$E$6:$E$23,"Víctor")+COUNTIFS('S8'!$B$6:$B$23,$A69,'S8'!$E$6:$E$23,"Ambos")+COUNTIFS('S9'!$B$6:$B$15,$A69,'S9'!$E$6:$E$15,"Víctor")+COUNTIFS('S9'!$B$6:$B$15,$A69,'S9'!$E$6:$E$15,"Ambos")+COUNTIFS('S10'!$B$6:$B$13,$A69,'S10'!$E$6:$E$13,"Víctor")+COUNTIFS('S10'!$B$6:$B$13,$A69,'S10'!$E$6:$E$13,"Ambos")+COUNTIFS('Holgura'!$B$6:$B$11,$A69,'Holgura'!$E$6:$E$11,"Víctor")+COUNTIFS('Holgura'!$B$6:$B$11,$A69,'Holgura'!$E$6:$E$11,"Ambos")+COUNTIFS('Entrega'!$B$6:$B$9,$A69,'Entrega'!$E$6:$E$9,"Víctor")+COUNTIFS('Entrega'!$B$6:$B$9,$A69,'Entrega'!$E$6:$E$9,"Ambos")+COUNTIFS('Defensa'!$B$6:$B$10,$A69,'Defensa'!$E$6:$E$10,"Víctor")+COUNTIFS('Defensa'!$B$6:$B$10,$A69,'Defensa'!$E$6:$E$10,"Ambos")</f>
+        <f>COUNTIFS('S1'!$B$6:$B$32,$A69,'S1'!$E$6:$E$32,"Víctor")+COUNTIFS('S1'!$B$6:$B$32,$A69,'S1'!$E$6:$E$32,"Ambos")+COUNTIFS('S2'!$B$6:$B$23,$A69,'S2'!$E$6:$E$23,"Víctor")+COUNTIFS('S2'!$B$6:$B$23,$A69,'S2'!$E$6:$E$23,"Ambos")+COUNTIFS('S3'!$B$6:$B$24,$A69,'S3'!$E$6:$E$24,"Víctor")+COUNTIFS('S3'!$B$6:$B$24,$A69,'S3'!$E$6:$E$24,"Ambos")+COUNTIFS('S4'!$B$6:$B$22,$A69,'S4'!$E$6:$E$22,"Víctor")+COUNTIFS('S4'!$B$6:$B$22,$A69,'S4'!$E$6:$E$22,"Ambos")+COUNTIFS('S5'!$B$6:$B$20,$A69,'S5'!$E$6:$E$20,"Víctor")+COUNTIFS('S5'!$B$6:$B$20,$A69,'S5'!$E$6:$E$20,"Ambos")+COUNTIFS('S6'!$B$6:$B$17,$A69,'S6'!$E$6:$E$17,"Víctor")+COUNTIFS('S6'!$B$6:$B$17,$A69,'S6'!$E$6:$E$17,"Ambos")+COUNTIFS('S7'!$B$6:$B$19,$A69,'S7'!$E$6:$E$19,"Víctor")+COUNTIFS('S7'!$B$6:$B$19,$A69,'S7'!$E$6:$E$19,"Ambos")+COUNTIFS('S8'!$B$6:$B$23,$A69,'S8'!$E$6:$E$23,"Víctor")+COUNTIFS('S8'!$B$6:$B$23,$A69,'S8'!$E$6:$E$23,"Ambos")+COUNTIFS('S9'!$B$6:$B$15,$A69,'S9'!$E$6:$E$15,"Víctor")+COUNTIFS('S9'!$B$6:$B$15,$A69,'S9'!$E$6:$E$15,"Ambos")+COUNTIFS('S10'!$B$6:$B$13,$A69,'S10'!$E$6:$E$13,"Víctor")+COUNTIFS('S10'!$B$6:$B$13,$A69,'S10'!$E$6:$E$13,"Ambos")+COUNTIFS('Holgura'!$B$6:$B$11,$A69,'Holgura'!$E$6:$E$11,"Víctor")+COUNTIFS('Holgura'!$B$6:$B$11,$A69,'Holgura'!$E$6:$E$11,"Ambos")+COUNTIFS('Entrega'!$B$6:$B$9,$A69,'Entrega'!$E$6:$E$9,"Víctor")+COUNTIFS('Entrega'!$B$6:$B$9,$A69,'Entrega'!$E$6:$E$9,"Ambos")+COUNTIFS('Defensa'!$B$6:$B$10,$A69,'Defensa'!$E$6:$E$10,"Víctor")+COUNTIFS('Defensa'!$B$6:$B$10,$A69,'Defensa'!$E$6:$E$10,"Ambos")</f>
         <v/>
       </c>
       <c r="G69" s="21">
-        <f>COUNTIFS('S1'!$B$6:$B$32,$A69,'S1'!$E$6:$E$32,"Diego")+COUNTIFS('S1'!$B$6:$B$32,$A69,'S1'!$E$6:$E$32,"Ambos")+COUNTIFS('S2'!$B$6:$B$23,$A69,'S2'!$E$6:$E$23,"Diego")+COUNTIFS('S2'!$B$6:$B$23,$A69,'S2'!$E$6:$E$23,"Ambos")+COUNTIFS('S3'!$B$6:$B$19,$A69,'S3'!$E$6:$E$19,"Diego")+COUNTIFS('S3'!$B$6:$B$19,$A69,'S3'!$E$6:$E$19,"Ambos")+COUNTIFS('S4'!$B$6:$B$20,$A69,'S4'!$E$6:$E$20,"Diego")+COUNTIFS('S4'!$B$6:$B$20,$A69,'S4'!$E$6:$E$20,"Ambos")+COUNTIFS('S5'!$B$6:$B$20,$A69,'S5'!$E$6:$E$20,"Diego")+COUNTIFS('S5'!$B$6:$B$20,$A69,'S5'!$E$6:$E$20,"Ambos")+COUNTIFS('S6'!$B$6:$B$17,$A69,'S6'!$E$6:$E$17,"Diego")+COUNTIFS('S6'!$B$6:$B$17,$A69,'S6'!$E$6:$E$17,"Ambos")+COUNTIFS('S7'!$B$6:$B$19,$A69,'S7'!$E$6:$E$19,"Diego")+COUNTIFS('S7'!$B$6:$B$19,$A69,'S7'!$E$6:$E$19,"Ambos")+COUNTIFS('S8'!$B$6:$B$23,$A69,'S8'!$E$6:$E$23,"Diego")+COUNTIFS('S8'!$B$6:$B$23,$A69,'S8'!$E$6:$E$23,"Ambos")+COUNTIFS('S9'!$B$6:$B$15,$A69,'S9'!$E$6:$E$15,"Diego")+COUNTIFS('S9'!$B$6:$B$15,$A69,'S9'!$E$6:$E$15,"Ambos")+COUNTIFS('S10'!$B$6:$B$13,$A69,'S10'!$E$6:$E$13,"Diego")+COUNTIFS('S10'!$B$6:$B$13,$A69,'S10'!$E$6:$E$13,"Ambos")+COUNTIFS('Holgura'!$B$6:$B$11,$A69,'Holgura'!$E$6:$E$11,"Diego")+COUNTIFS('Holgura'!$B$6:$B$11,$A69,'Holgura'!$E$6:$E$11,"Ambos")+COUNTIFS('Entrega'!$B$6:$B$9,$A69,'Entrega'!$E$6:$E$9,"Diego")+COUNTIFS('Entrega'!$B$6:$B$9,$A69,'Entrega'!$E$6:$E$9,"Ambos")+COUNTIFS('Defensa'!$B$6:$B$10,$A69,'Defensa'!$E$6:$E$10,"Diego")+COUNTIFS('Defensa'!$B$6:$B$10,$A69,'Defensa'!$E$6:$E$10,"Ambos")</f>
+        <f>COUNTIFS('S1'!$B$6:$B$32,$A69,'S1'!$E$6:$E$32,"Diego")+COUNTIFS('S1'!$B$6:$B$32,$A69,'S1'!$E$6:$E$32,"Ambos")+COUNTIFS('S2'!$B$6:$B$23,$A69,'S2'!$E$6:$E$23,"Diego")+COUNTIFS('S2'!$B$6:$B$23,$A69,'S2'!$E$6:$E$23,"Ambos")+COUNTIFS('S3'!$B$6:$B$24,$A69,'S3'!$E$6:$E$24,"Diego")+COUNTIFS('S3'!$B$6:$B$24,$A69,'S3'!$E$6:$E$24,"Ambos")+COUNTIFS('S4'!$B$6:$B$22,$A69,'S4'!$E$6:$E$22,"Diego")+COUNTIFS('S4'!$B$6:$B$22,$A69,'S4'!$E$6:$E$22,"Ambos")+COUNTIFS('S5'!$B$6:$B$20,$A69,'S5'!$E$6:$E$20,"Diego")+COUNTIFS('S5'!$B$6:$B$20,$A69,'S5'!$E$6:$E$20,"Ambos")+COUNTIFS('S6'!$B$6:$B$17,$A69,'S6'!$E$6:$E$17,"Diego")+COUNTIFS('S6'!$B$6:$B$17,$A69,'S6'!$E$6:$E$17,"Ambos")+COUNTIFS('S7'!$B$6:$B$19,$A69,'S7'!$E$6:$E$19,"Diego")+COUNTIFS('S7'!$B$6:$B$19,$A69,'S7'!$E$6:$E$19,"Ambos")+COUNTIFS('S8'!$B$6:$B$23,$A69,'S8'!$E$6:$E$23,"Diego")+COUNTIFS('S8'!$B$6:$B$23,$A69,'S8'!$E$6:$E$23,"Ambos")+COUNTIFS('S9'!$B$6:$B$15,$A69,'S9'!$E$6:$E$15,"Diego")+COUNTIFS('S9'!$B$6:$B$15,$A69,'S9'!$E$6:$E$15,"Ambos")+COUNTIFS('S10'!$B$6:$B$13,$A69,'S10'!$E$6:$E$13,"Diego")+COUNTIFS('S10'!$B$6:$B$13,$A69,'S10'!$E$6:$E$13,"Ambos")+COUNTIFS('Holgura'!$B$6:$B$11,$A69,'Holgura'!$E$6:$E$11,"Diego")+COUNTIFS('Holgura'!$B$6:$B$11,$A69,'Holgura'!$E$6:$E$11,"Ambos")+COUNTIFS('Entrega'!$B$6:$B$9,$A69,'Entrega'!$E$6:$E$9,"Diego")+COUNTIFS('Entrega'!$B$6:$B$9,$A69,'Entrega'!$E$6:$E$9,"Ambos")+COUNTIFS('Defensa'!$B$6:$B$10,$A69,'Defensa'!$E$6:$E$10,"Diego")+COUNTIFS('Defensa'!$B$6:$B$10,$A69,'Defensa'!$E$6:$E$10,"Ambos")</f>
         <v/>
       </c>
     </row>
@@ -10565,19 +10586,19 @@
         <v/>
       </c>
       <c r="D70" s="21">
-        <f>SUMIFS('S1'!$I$6:$I$32,'S1'!$B$6:$B$32,$A70,'S1'!$E$6:$E$32,"Víctor")+SUMIFS('S1'!$I$6:$I$32,'S1'!$B$6:$B$32,$A70,'S1'!$E$6:$E$32,"Ambos")+SUMIFS('S2'!$I$6:$I$23,'S2'!$B$6:$B$23,$A70,'S2'!$E$6:$E$23,"Víctor")+SUMIFS('S2'!$I$6:$I$23,'S2'!$B$6:$B$23,$A70,'S2'!$E$6:$E$23,"Ambos")+SUMIFS('S3'!$I$6:$I$19,'S3'!$B$6:$B$19,$A70,'S3'!$E$6:$E$19,"Víctor")+SUMIFS('S3'!$I$6:$I$19,'S3'!$B$6:$B$19,$A70,'S3'!$E$6:$E$19,"Ambos")+SUMIFS('S4'!$I$6:$I$20,'S4'!$B$6:$B$20,$A70,'S4'!$E$6:$E$20,"Víctor")+SUMIFS('S4'!$I$6:$I$20,'S4'!$B$6:$B$20,$A70,'S4'!$E$6:$E$20,"Ambos")+SUMIFS('S5'!$I$6:$I$20,'S5'!$B$6:$B$20,$A70,'S5'!$E$6:$E$20,"Víctor")+SUMIFS('S5'!$I$6:$I$20,'S5'!$B$6:$B$20,$A70,'S5'!$E$6:$E$20,"Ambos")+SUMIFS('S6'!$I$6:$I$17,'S6'!$B$6:$B$17,$A70,'S6'!$E$6:$E$17,"Víctor")+SUMIFS('S6'!$I$6:$I$17,'S6'!$B$6:$B$17,$A70,'S6'!$E$6:$E$17,"Ambos")+SUMIFS('S7'!$I$6:$I$19,'S7'!$B$6:$B$19,$A70,'S7'!$E$6:$E$19,"Víctor")+SUMIFS('S7'!$I$6:$I$19,'S7'!$B$6:$B$19,$A70,'S7'!$E$6:$E$19,"Ambos")+SUMIFS('S8'!$I$6:$I$23,'S8'!$B$6:$B$23,$A70,'S8'!$E$6:$E$23,"Víctor")+SUMIFS('S8'!$I$6:$I$23,'S8'!$B$6:$B$23,$A70,'S8'!$E$6:$E$23,"Ambos")+SUMIFS('S9'!$I$6:$I$15,'S9'!$B$6:$B$15,$A70,'S9'!$E$6:$E$15,"Víctor")+SUMIFS('S9'!$I$6:$I$15,'S9'!$B$6:$B$15,$A70,'S9'!$E$6:$E$15,"Ambos")+SUMIFS('S10'!$I$6:$I$13,'S10'!$B$6:$B$13,$A70,'S10'!$E$6:$E$13,"Víctor")+SUMIFS('S10'!$I$6:$I$13,'S10'!$B$6:$B$13,$A70,'S10'!$E$6:$E$13,"Ambos")+SUMIFS('Holgura'!$I$6:$I$11,'Holgura'!$B$6:$B$11,$A70,'Holgura'!$E$6:$E$11,"Víctor")+SUMIFS('Holgura'!$I$6:$I$11,'Holgura'!$B$6:$B$11,$A70,'Holgura'!$E$6:$E$11,"Ambos")+SUMIFS('Entrega'!$I$6:$I$9,'Entrega'!$B$6:$B$9,$A70,'Entrega'!$E$6:$E$9,"Víctor")+SUMIFS('Entrega'!$I$6:$I$9,'Entrega'!$B$6:$B$9,$A70,'Entrega'!$E$6:$E$9,"Ambos")+SUMIFS('Defensa'!$I$6:$I$10,'Defensa'!$B$6:$B$10,$A70,'Defensa'!$E$6:$E$10,"Víctor")+SUMIFS('Defensa'!$I$6:$I$10,'Defensa'!$B$6:$B$10,$A70,'Defensa'!$E$6:$E$10,"Ambos")</f>
+        <f>SUMIFS('S1'!$I$6:$I$32,'S1'!$B$6:$B$32,$A70,'S1'!$E$6:$E$32,"Víctor")+SUMIFS('S1'!$I$6:$I$32,'S1'!$B$6:$B$32,$A70,'S1'!$E$6:$E$32,"Ambos")+SUMIFS('S2'!$I$6:$I$23,'S2'!$B$6:$B$23,$A70,'S2'!$E$6:$E$23,"Víctor")+SUMIFS('S2'!$I$6:$I$23,'S2'!$B$6:$B$23,$A70,'S2'!$E$6:$E$23,"Ambos")+SUMIFS('S3'!$I$6:$I$24,'S3'!$B$6:$B$24,$A70,'S3'!$E$6:$E$24,"Víctor")+SUMIFS('S3'!$I$6:$I$24,'S3'!$B$6:$B$24,$A70,'S3'!$E$6:$E$24,"Ambos")+SUMIFS('S4'!$I$6:$I$22,'S4'!$B$6:$B$22,$A70,'S4'!$E$6:$E$22,"Víctor")+SUMIFS('S4'!$I$6:$I$22,'S4'!$B$6:$B$22,$A70,'S4'!$E$6:$E$22,"Ambos")+SUMIFS('S5'!$I$6:$I$20,'S5'!$B$6:$B$20,$A70,'S5'!$E$6:$E$20,"Víctor")+SUMIFS('S5'!$I$6:$I$20,'S5'!$B$6:$B$20,$A70,'S5'!$E$6:$E$20,"Ambos")+SUMIFS('S6'!$I$6:$I$17,'S6'!$B$6:$B$17,$A70,'S6'!$E$6:$E$17,"Víctor")+SUMIFS('S6'!$I$6:$I$17,'S6'!$B$6:$B$17,$A70,'S6'!$E$6:$E$17,"Ambos")+SUMIFS('S7'!$I$6:$I$19,'S7'!$B$6:$B$19,$A70,'S7'!$E$6:$E$19,"Víctor")+SUMIFS('S7'!$I$6:$I$19,'S7'!$B$6:$B$19,$A70,'S7'!$E$6:$E$19,"Ambos")+SUMIFS('S8'!$I$6:$I$23,'S8'!$B$6:$B$23,$A70,'S8'!$E$6:$E$23,"Víctor")+SUMIFS('S8'!$I$6:$I$23,'S8'!$B$6:$B$23,$A70,'S8'!$E$6:$E$23,"Ambos")+SUMIFS('S9'!$I$6:$I$15,'S9'!$B$6:$B$15,$A70,'S9'!$E$6:$E$15,"Víctor")+SUMIFS('S9'!$I$6:$I$15,'S9'!$B$6:$B$15,$A70,'S9'!$E$6:$E$15,"Ambos")+SUMIFS('S10'!$I$6:$I$13,'S10'!$B$6:$B$13,$A70,'S10'!$E$6:$E$13,"Víctor")+SUMIFS('S10'!$I$6:$I$13,'S10'!$B$6:$B$13,$A70,'S10'!$E$6:$E$13,"Ambos")+SUMIFS('Holgura'!$I$6:$I$11,'Holgura'!$B$6:$B$11,$A70,'Holgura'!$E$6:$E$11,"Víctor")+SUMIFS('Holgura'!$I$6:$I$11,'Holgura'!$B$6:$B$11,$A70,'Holgura'!$E$6:$E$11,"Ambos")+SUMIFS('Entrega'!$I$6:$I$9,'Entrega'!$B$6:$B$9,$A70,'Entrega'!$E$6:$E$9,"Víctor")+SUMIFS('Entrega'!$I$6:$I$9,'Entrega'!$B$6:$B$9,$A70,'Entrega'!$E$6:$E$9,"Ambos")+SUMIFS('Defensa'!$I$6:$I$10,'Defensa'!$B$6:$B$10,$A70,'Defensa'!$E$6:$E$10,"Víctor")+SUMIFS('Defensa'!$I$6:$I$10,'Defensa'!$B$6:$B$10,$A70,'Defensa'!$E$6:$E$10,"Ambos")</f>
         <v/>
       </c>
       <c r="E70" s="21">
-        <f>SUMIFS('S1'!$I$6:$I$32,'S1'!$B$6:$B$32,$A70,'S1'!$E$6:$E$32,"Diego")+SUMIFS('S1'!$I$6:$I$32,'S1'!$B$6:$B$32,$A70,'S1'!$E$6:$E$32,"Ambos")+SUMIFS('S2'!$I$6:$I$23,'S2'!$B$6:$B$23,$A70,'S2'!$E$6:$E$23,"Diego")+SUMIFS('S2'!$I$6:$I$23,'S2'!$B$6:$B$23,$A70,'S2'!$E$6:$E$23,"Ambos")+SUMIFS('S3'!$I$6:$I$19,'S3'!$B$6:$B$19,$A70,'S3'!$E$6:$E$19,"Diego")+SUMIFS('S3'!$I$6:$I$19,'S3'!$B$6:$B$19,$A70,'S3'!$E$6:$E$19,"Ambos")+SUMIFS('S4'!$I$6:$I$20,'S4'!$B$6:$B$20,$A70,'S4'!$E$6:$E$20,"Diego")+SUMIFS('S4'!$I$6:$I$20,'S4'!$B$6:$B$20,$A70,'S4'!$E$6:$E$20,"Ambos")+SUMIFS('S5'!$I$6:$I$20,'S5'!$B$6:$B$20,$A70,'S5'!$E$6:$E$20,"Diego")+SUMIFS('S5'!$I$6:$I$20,'S5'!$B$6:$B$20,$A70,'S5'!$E$6:$E$20,"Ambos")+SUMIFS('S6'!$I$6:$I$17,'S6'!$B$6:$B$17,$A70,'S6'!$E$6:$E$17,"Diego")+SUMIFS('S6'!$I$6:$I$17,'S6'!$B$6:$B$17,$A70,'S6'!$E$6:$E$17,"Ambos")+SUMIFS('S7'!$I$6:$I$19,'S7'!$B$6:$B$19,$A70,'S7'!$E$6:$E$19,"Diego")+SUMIFS('S7'!$I$6:$I$19,'S7'!$B$6:$B$19,$A70,'S7'!$E$6:$E$19,"Ambos")+SUMIFS('S8'!$I$6:$I$23,'S8'!$B$6:$B$23,$A70,'S8'!$E$6:$E$23,"Diego")+SUMIFS('S8'!$I$6:$I$23,'S8'!$B$6:$B$23,$A70,'S8'!$E$6:$E$23,"Ambos")+SUMIFS('S9'!$I$6:$I$15,'S9'!$B$6:$B$15,$A70,'S9'!$E$6:$E$15,"Diego")+SUMIFS('S9'!$I$6:$I$15,'S9'!$B$6:$B$15,$A70,'S9'!$E$6:$E$15,"Ambos")+SUMIFS('S10'!$I$6:$I$13,'S10'!$B$6:$B$13,$A70,'S10'!$E$6:$E$13,"Diego")+SUMIFS('S10'!$I$6:$I$13,'S10'!$B$6:$B$13,$A70,'S10'!$E$6:$E$13,"Ambos")+SUMIFS('Holgura'!$I$6:$I$11,'Holgura'!$B$6:$B$11,$A70,'Holgura'!$E$6:$E$11,"Diego")+SUMIFS('Holgura'!$I$6:$I$11,'Holgura'!$B$6:$B$11,$A70,'Holgura'!$E$6:$E$11,"Ambos")+SUMIFS('Entrega'!$I$6:$I$9,'Entrega'!$B$6:$B$9,$A70,'Entrega'!$E$6:$E$9,"Diego")+SUMIFS('Entrega'!$I$6:$I$9,'Entrega'!$B$6:$B$9,$A70,'Entrega'!$E$6:$E$9,"Ambos")+SUMIFS('Defensa'!$I$6:$I$10,'Defensa'!$B$6:$B$10,$A70,'Defensa'!$E$6:$E$10,"Diego")+SUMIFS('Defensa'!$I$6:$I$10,'Defensa'!$B$6:$B$10,$A70,'Defensa'!$E$6:$E$10,"Ambos")</f>
+        <f>SUMIFS('S1'!$I$6:$I$32,'S1'!$B$6:$B$32,$A70,'S1'!$E$6:$E$32,"Diego")+SUMIFS('S1'!$I$6:$I$32,'S1'!$B$6:$B$32,$A70,'S1'!$E$6:$E$32,"Ambos")+SUMIFS('S2'!$I$6:$I$23,'S2'!$B$6:$B$23,$A70,'S2'!$E$6:$E$23,"Diego")+SUMIFS('S2'!$I$6:$I$23,'S2'!$B$6:$B$23,$A70,'S2'!$E$6:$E$23,"Ambos")+SUMIFS('S3'!$I$6:$I$24,'S3'!$B$6:$B$24,$A70,'S3'!$E$6:$E$24,"Diego")+SUMIFS('S3'!$I$6:$I$24,'S3'!$B$6:$B$24,$A70,'S3'!$E$6:$E$24,"Ambos")+SUMIFS('S4'!$I$6:$I$22,'S4'!$B$6:$B$22,$A70,'S4'!$E$6:$E$22,"Diego")+SUMIFS('S4'!$I$6:$I$22,'S4'!$B$6:$B$22,$A70,'S4'!$E$6:$E$22,"Ambos")+SUMIFS('S5'!$I$6:$I$20,'S5'!$B$6:$B$20,$A70,'S5'!$E$6:$E$20,"Diego")+SUMIFS('S5'!$I$6:$I$20,'S5'!$B$6:$B$20,$A70,'S5'!$E$6:$E$20,"Ambos")+SUMIFS('S6'!$I$6:$I$17,'S6'!$B$6:$B$17,$A70,'S6'!$E$6:$E$17,"Diego")+SUMIFS('S6'!$I$6:$I$17,'S6'!$B$6:$B$17,$A70,'S6'!$E$6:$E$17,"Ambos")+SUMIFS('S7'!$I$6:$I$19,'S7'!$B$6:$B$19,$A70,'S7'!$E$6:$E$19,"Diego")+SUMIFS('S7'!$I$6:$I$19,'S7'!$B$6:$B$19,$A70,'S7'!$E$6:$E$19,"Ambos")+SUMIFS('S8'!$I$6:$I$23,'S8'!$B$6:$B$23,$A70,'S8'!$E$6:$E$23,"Diego")+SUMIFS('S8'!$I$6:$I$23,'S8'!$B$6:$B$23,$A70,'S8'!$E$6:$E$23,"Ambos")+SUMIFS('S9'!$I$6:$I$15,'S9'!$B$6:$B$15,$A70,'S9'!$E$6:$E$15,"Diego")+SUMIFS('S9'!$I$6:$I$15,'S9'!$B$6:$B$15,$A70,'S9'!$E$6:$E$15,"Ambos")+SUMIFS('S10'!$I$6:$I$13,'S10'!$B$6:$B$13,$A70,'S10'!$E$6:$E$13,"Diego")+SUMIFS('S10'!$I$6:$I$13,'S10'!$B$6:$B$13,$A70,'S10'!$E$6:$E$13,"Ambos")+SUMIFS('Holgura'!$I$6:$I$11,'Holgura'!$B$6:$B$11,$A70,'Holgura'!$E$6:$E$11,"Diego")+SUMIFS('Holgura'!$I$6:$I$11,'Holgura'!$B$6:$B$11,$A70,'Holgura'!$E$6:$E$11,"Ambos")+SUMIFS('Entrega'!$I$6:$I$9,'Entrega'!$B$6:$B$9,$A70,'Entrega'!$E$6:$E$9,"Diego")+SUMIFS('Entrega'!$I$6:$I$9,'Entrega'!$B$6:$B$9,$A70,'Entrega'!$E$6:$E$9,"Ambos")+SUMIFS('Defensa'!$I$6:$I$10,'Defensa'!$B$6:$B$10,$A70,'Defensa'!$E$6:$E$10,"Diego")+SUMIFS('Defensa'!$I$6:$I$10,'Defensa'!$B$6:$B$10,$A70,'Defensa'!$E$6:$E$10,"Ambos")</f>
         <v/>
       </c>
       <c r="F70" s="21">
-        <f>COUNTIFS('S1'!$B$6:$B$32,$A70,'S1'!$E$6:$E$32,"Víctor")+COUNTIFS('S1'!$B$6:$B$32,$A70,'S1'!$E$6:$E$32,"Ambos")+COUNTIFS('S2'!$B$6:$B$23,$A70,'S2'!$E$6:$E$23,"Víctor")+COUNTIFS('S2'!$B$6:$B$23,$A70,'S2'!$E$6:$E$23,"Ambos")+COUNTIFS('S3'!$B$6:$B$19,$A70,'S3'!$E$6:$E$19,"Víctor")+COUNTIFS('S3'!$B$6:$B$19,$A70,'S3'!$E$6:$E$19,"Ambos")+COUNTIFS('S4'!$B$6:$B$20,$A70,'S4'!$E$6:$E$20,"Víctor")+COUNTIFS('S4'!$B$6:$B$20,$A70,'S4'!$E$6:$E$20,"Ambos")+COUNTIFS('S5'!$B$6:$B$20,$A70,'S5'!$E$6:$E$20,"Víctor")+COUNTIFS('S5'!$B$6:$B$20,$A70,'S5'!$E$6:$E$20,"Ambos")+COUNTIFS('S6'!$B$6:$B$17,$A70,'S6'!$E$6:$E$17,"Víctor")+COUNTIFS('S6'!$B$6:$B$17,$A70,'S6'!$E$6:$E$17,"Ambos")+COUNTIFS('S7'!$B$6:$B$19,$A70,'S7'!$E$6:$E$19,"Víctor")+COUNTIFS('S7'!$B$6:$B$19,$A70,'S7'!$E$6:$E$19,"Ambos")+COUNTIFS('S8'!$B$6:$B$23,$A70,'S8'!$E$6:$E$23,"Víctor")+COUNTIFS('S8'!$B$6:$B$23,$A70,'S8'!$E$6:$E$23,"Ambos")+COUNTIFS('S9'!$B$6:$B$15,$A70,'S9'!$E$6:$E$15,"Víctor")+COUNTIFS('S9'!$B$6:$B$15,$A70,'S9'!$E$6:$E$15,"Ambos")+COUNTIFS('S10'!$B$6:$B$13,$A70,'S10'!$E$6:$E$13,"Víctor")+COUNTIFS('S10'!$B$6:$B$13,$A70,'S10'!$E$6:$E$13,"Ambos")+COUNTIFS('Holgura'!$B$6:$B$11,$A70,'Holgura'!$E$6:$E$11,"Víctor")+COUNTIFS('Holgura'!$B$6:$B$11,$A70,'Holgura'!$E$6:$E$11,"Ambos")+COUNTIFS('Entrega'!$B$6:$B$9,$A70,'Entrega'!$E$6:$E$9,"Víctor")+COUNTIFS('Entrega'!$B$6:$B$9,$A70,'Entrega'!$E$6:$E$9,"Ambos")+COUNTIFS('Defensa'!$B$6:$B$10,$A70,'Defensa'!$E$6:$E$10,"Víctor")+COUNTIFS('Defensa'!$B$6:$B$10,$A70,'Defensa'!$E$6:$E$10,"Ambos")</f>
+        <f>COUNTIFS('S1'!$B$6:$B$32,$A70,'S1'!$E$6:$E$32,"Víctor")+COUNTIFS('S1'!$B$6:$B$32,$A70,'S1'!$E$6:$E$32,"Ambos")+COUNTIFS('S2'!$B$6:$B$23,$A70,'S2'!$E$6:$E$23,"Víctor")+COUNTIFS('S2'!$B$6:$B$23,$A70,'S2'!$E$6:$E$23,"Ambos")+COUNTIFS('S3'!$B$6:$B$24,$A70,'S3'!$E$6:$E$24,"Víctor")+COUNTIFS('S3'!$B$6:$B$24,$A70,'S3'!$E$6:$E$24,"Ambos")+COUNTIFS('S4'!$B$6:$B$22,$A70,'S4'!$E$6:$E$22,"Víctor")+COUNTIFS('S4'!$B$6:$B$22,$A70,'S4'!$E$6:$E$22,"Ambos")+COUNTIFS('S5'!$B$6:$B$20,$A70,'S5'!$E$6:$E$20,"Víctor")+COUNTIFS('S5'!$B$6:$B$20,$A70,'S5'!$E$6:$E$20,"Ambos")+COUNTIFS('S6'!$B$6:$B$17,$A70,'S6'!$E$6:$E$17,"Víctor")+COUNTIFS('S6'!$B$6:$B$17,$A70,'S6'!$E$6:$E$17,"Ambos")+COUNTIFS('S7'!$B$6:$B$19,$A70,'S7'!$E$6:$E$19,"Víctor")+COUNTIFS('S7'!$B$6:$B$19,$A70,'S7'!$E$6:$E$19,"Ambos")+COUNTIFS('S8'!$B$6:$B$23,$A70,'S8'!$E$6:$E$23,"Víctor")+COUNTIFS('S8'!$B$6:$B$23,$A70,'S8'!$E$6:$E$23,"Ambos")+COUNTIFS('S9'!$B$6:$B$15,$A70,'S9'!$E$6:$E$15,"Víctor")+COUNTIFS('S9'!$B$6:$B$15,$A70,'S9'!$E$6:$E$15,"Ambos")+COUNTIFS('S10'!$B$6:$B$13,$A70,'S10'!$E$6:$E$13,"Víctor")+COUNTIFS('S10'!$B$6:$B$13,$A70,'S10'!$E$6:$E$13,"Ambos")+COUNTIFS('Holgura'!$B$6:$B$11,$A70,'Holgura'!$E$6:$E$11,"Víctor")+COUNTIFS('Holgura'!$B$6:$B$11,$A70,'Holgura'!$E$6:$E$11,"Ambos")+COUNTIFS('Entrega'!$B$6:$B$9,$A70,'Entrega'!$E$6:$E$9,"Víctor")+COUNTIFS('Entrega'!$B$6:$B$9,$A70,'Entrega'!$E$6:$E$9,"Ambos")+COUNTIFS('Defensa'!$B$6:$B$10,$A70,'Defensa'!$E$6:$E$10,"Víctor")+COUNTIFS('Defensa'!$B$6:$B$10,$A70,'Defensa'!$E$6:$E$10,"Ambos")</f>
         <v/>
       </c>
       <c r="G70" s="21">
-        <f>COUNTIFS('S1'!$B$6:$B$32,$A70,'S1'!$E$6:$E$32,"Diego")+COUNTIFS('S1'!$B$6:$B$32,$A70,'S1'!$E$6:$E$32,"Ambos")+COUNTIFS('S2'!$B$6:$B$23,$A70,'S2'!$E$6:$E$23,"Diego")+COUNTIFS('S2'!$B$6:$B$23,$A70,'S2'!$E$6:$E$23,"Ambos")+COUNTIFS('S3'!$B$6:$B$19,$A70,'S3'!$E$6:$E$19,"Diego")+COUNTIFS('S3'!$B$6:$B$19,$A70,'S3'!$E$6:$E$19,"Ambos")+COUNTIFS('S4'!$B$6:$B$20,$A70,'S4'!$E$6:$E$20,"Diego")+COUNTIFS('S4'!$B$6:$B$20,$A70,'S4'!$E$6:$E$20,"Ambos")+COUNTIFS('S5'!$B$6:$B$20,$A70,'S5'!$E$6:$E$20,"Diego")+COUNTIFS('S5'!$B$6:$B$20,$A70,'S5'!$E$6:$E$20,"Ambos")+COUNTIFS('S6'!$B$6:$B$17,$A70,'S6'!$E$6:$E$17,"Diego")+COUNTIFS('S6'!$B$6:$B$17,$A70,'S6'!$E$6:$E$17,"Ambos")+COUNTIFS('S7'!$B$6:$B$19,$A70,'S7'!$E$6:$E$19,"Diego")+COUNTIFS('S7'!$B$6:$B$19,$A70,'S7'!$E$6:$E$19,"Ambos")+COUNTIFS('S8'!$B$6:$B$23,$A70,'S8'!$E$6:$E$23,"Diego")+COUNTIFS('S8'!$B$6:$B$23,$A70,'S8'!$E$6:$E$23,"Ambos")+COUNTIFS('S9'!$B$6:$B$15,$A70,'S9'!$E$6:$E$15,"Diego")+COUNTIFS('S9'!$B$6:$B$15,$A70,'S9'!$E$6:$E$15,"Ambos")+COUNTIFS('S10'!$B$6:$B$13,$A70,'S10'!$E$6:$E$13,"Diego")+COUNTIFS('S10'!$B$6:$B$13,$A70,'S10'!$E$6:$E$13,"Ambos")+COUNTIFS('Holgura'!$B$6:$B$11,$A70,'Holgura'!$E$6:$E$11,"Diego")+COUNTIFS('Holgura'!$B$6:$B$11,$A70,'Holgura'!$E$6:$E$11,"Ambos")+COUNTIFS('Entrega'!$B$6:$B$9,$A70,'Entrega'!$E$6:$E$9,"Diego")+COUNTIFS('Entrega'!$B$6:$B$9,$A70,'Entrega'!$E$6:$E$9,"Ambos")+COUNTIFS('Defensa'!$B$6:$B$10,$A70,'Defensa'!$E$6:$E$10,"Diego")+COUNTIFS('Defensa'!$B$6:$B$10,$A70,'Defensa'!$E$6:$E$10,"Ambos")</f>
+        <f>COUNTIFS('S1'!$B$6:$B$32,$A70,'S1'!$E$6:$E$32,"Diego")+COUNTIFS('S1'!$B$6:$B$32,$A70,'S1'!$E$6:$E$32,"Ambos")+COUNTIFS('S2'!$B$6:$B$23,$A70,'S2'!$E$6:$E$23,"Diego")+COUNTIFS('S2'!$B$6:$B$23,$A70,'S2'!$E$6:$E$23,"Ambos")+COUNTIFS('S3'!$B$6:$B$24,$A70,'S3'!$E$6:$E$24,"Diego")+COUNTIFS('S3'!$B$6:$B$24,$A70,'S3'!$E$6:$E$24,"Ambos")+COUNTIFS('S4'!$B$6:$B$22,$A70,'S4'!$E$6:$E$22,"Diego")+COUNTIFS('S4'!$B$6:$B$22,$A70,'S4'!$E$6:$E$22,"Ambos")+COUNTIFS('S5'!$B$6:$B$20,$A70,'S5'!$E$6:$E$20,"Diego")+COUNTIFS('S5'!$B$6:$B$20,$A70,'S5'!$E$6:$E$20,"Ambos")+COUNTIFS('S6'!$B$6:$B$17,$A70,'S6'!$E$6:$E$17,"Diego")+COUNTIFS('S6'!$B$6:$B$17,$A70,'S6'!$E$6:$E$17,"Ambos")+COUNTIFS('S7'!$B$6:$B$19,$A70,'S7'!$E$6:$E$19,"Diego")+COUNTIFS('S7'!$B$6:$B$19,$A70,'S7'!$E$6:$E$19,"Ambos")+COUNTIFS('S8'!$B$6:$B$23,$A70,'S8'!$E$6:$E$23,"Diego")+COUNTIFS('S8'!$B$6:$B$23,$A70,'S8'!$E$6:$E$23,"Ambos")+COUNTIFS('S9'!$B$6:$B$15,$A70,'S9'!$E$6:$E$15,"Diego")+COUNTIFS('S9'!$B$6:$B$15,$A70,'S9'!$E$6:$E$15,"Ambos")+COUNTIFS('S10'!$B$6:$B$13,$A70,'S10'!$E$6:$E$13,"Diego")+COUNTIFS('S10'!$B$6:$B$13,$A70,'S10'!$E$6:$E$13,"Ambos")+COUNTIFS('Holgura'!$B$6:$B$11,$A70,'Holgura'!$E$6:$E$11,"Diego")+COUNTIFS('Holgura'!$B$6:$B$11,$A70,'Holgura'!$E$6:$E$11,"Ambos")+COUNTIFS('Entrega'!$B$6:$B$9,$A70,'Entrega'!$E$6:$E$9,"Diego")+COUNTIFS('Entrega'!$B$6:$B$9,$A70,'Entrega'!$E$6:$E$9,"Ambos")+COUNTIFS('Defensa'!$B$6:$B$10,$A70,'Defensa'!$E$6:$E$10,"Diego")+COUNTIFS('Defensa'!$B$6:$B$10,$A70,'Defensa'!$E$6:$E$10,"Ambos")</f>
         <v/>
       </c>
     </row>
@@ -10594,19 +10615,19 @@
         <v/>
       </c>
       <c r="D71" s="21">
-        <f>SUMIFS('S1'!$I$6:$I$32,'S1'!$B$6:$B$32,$A71,'S1'!$E$6:$E$32,"Víctor")+SUMIFS('S1'!$I$6:$I$32,'S1'!$B$6:$B$32,$A71,'S1'!$E$6:$E$32,"Ambos")+SUMIFS('S2'!$I$6:$I$23,'S2'!$B$6:$B$23,$A71,'S2'!$E$6:$E$23,"Víctor")+SUMIFS('S2'!$I$6:$I$23,'S2'!$B$6:$B$23,$A71,'S2'!$E$6:$E$23,"Ambos")+SUMIFS('S3'!$I$6:$I$19,'S3'!$B$6:$B$19,$A71,'S3'!$E$6:$E$19,"Víctor")+SUMIFS('S3'!$I$6:$I$19,'S3'!$B$6:$B$19,$A71,'S3'!$E$6:$E$19,"Ambos")+SUMIFS('S4'!$I$6:$I$20,'S4'!$B$6:$B$20,$A71,'S4'!$E$6:$E$20,"Víctor")+SUMIFS('S4'!$I$6:$I$20,'S4'!$B$6:$B$20,$A71,'S4'!$E$6:$E$20,"Ambos")+SUMIFS('S5'!$I$6:$I$20,'S5'!$B$6:$B$20,$A71,'S5'!$E$6:$E$20,"Víctor")+SUMIFS('S5'!$I$6:$I$20,'S5'!$B$6:$B$20,$A71,'S5'!$E$6:$E$20,"Ambos")+SUMIFS('S6'!$I$6:$I$17,'S6'!$B$6:$B$17,$A71,'S6'!$E$6:$E$17,"Víctor")+SUMIFS('S6'!$I$6:$I$17,'S6'!$B$6:$B$17,$A71,'S6'!$E$6:$E$17,"Ambos")+SUMIFS('S7'!$I$6:$I$19,'S7'!$B$6:$B$19,$A71,'S7'!$E$6:$E$19,"Víctor")+SUMIFS('S7'!$I$6:$I$19,'S7'!$B$6:$B$19,$A71,'S7'!$E$6:$E$19,"Ambos")+SUMIFS('S8'!$I$6:$I$23,'S8'!$B$6:$B$23,$A71,'S8'!$E$6:$E$23,"Víctor")+SUMIFS('S8'!$I$6:$I$23,'S8'!$B$6:$B$23,$A71,'S8'!$E$6:$E$23,"Ambos")+SUMIFS('S9'!$I$6:$I$15,'S9'!$B$6:$B$15,$A71,'S9'!$E$6:$E$15,"Víctor")+SUMIFS('S9'!$I$6:$I$15,'S9'!$B$6:$B$15,$A71,'S9'!$E$6:$E$15,"Ambos")+SUMIFS('S10'!$I$6:$I$13,'S10'!$B$6:$B$13,$A71,'S10'!$E$6:$E$13,"Víctor")+SUMIFS('S10'!$I$6:$I$13,'S10'!$B$6:$B$13,$A71,'S10'!$E$6:$E$13,"Ambos")+SUMIFS('Holgura'!$I$6:$I$11,'Holgura'!$B$6:$B$11,$A71,'Holgura'!$E$6:$E$11,"Víctor")+SUMIFS('Holgura'!$I$6:$I$11,'Holgura'!$B$6:$B$11,$A71,'Holgura'!$E$6:$E$11,"Ambos")+SUMIFS('Entrega'!$I$6:$I$9,'Entrega'!$B$6:$B$9,$A71,'Entrega'!$E$6:$E$9,"Víctor")+SUMIFS('Entrega'!$I$6:$I$9,'Entrega'!$B$6:$B$9,$A71,'Entrega'!$E$6:$E$9,"Ambos")+SUMIFS('Defensa'!$I$6:$I$10,'Defensa'!$B$6:$B$10,$A71,'Defensa'!$E$6:$E$10,"Víctor")+SUMIFS('Defensa'!$I$6:$I$10,'Defensa'!$B$6:$B$10,$A71,'Defensa'!$E$6:$E$10,"Ambos")</f>
+        <f>SUMIFS('S1'!$I$6:$I$32,'S1'!$B$6:$B$32,$A71,'S1'!$E$6:$E$32,"Víctor")+SUMIFS('S1'!$I$6:$I$32,'S1'!$B$6:$B$32,$A71,'S1'!$E$6:$E$32,"Ambos")+SUMIFS('S2'!$I$6:$I$23,'S2'!$B$6:$B$23,$A71,'S2'!$E$6:$E$23,"Víctor")+SUMIFS('S2'!$I$6:$I$23,'S2'!$B$6:$B$23,$A71,'S2'!$E$6:$E$23,"Ambos")+SUMIFS('S3'!$I$6:$I$24,'S3'!$B$6:$B$24,$A71,'S3'!$E$6:$E$24,"Víctor")+SUMIFS('S3'!$I$6:$I$24,'S3'!$B$6:$B$24,$A71,'S3'!$E$6:$E$24,"Ambos")+SUMIFS('S4'!$I$6:$I$22,'S4'!$B$6:$B$22,$A71,'S4'!$E$6:$E$22,"Víctor")+SUMIFS('S4'!$I$6:$I$22,'S4'!$B$6:$B$22,$A71,'S4'!$E$6:$E$22,"Ambos")+SUMIFS('S5'!$I$6:$I$20,'S5'!$B$6:$B$20,$A71,'S5'!$E$6:$E$20,"Víctor")+SUMIFS('S5'!$I$6:$I$20,'S5'!$B$6:$B$20,$A71,'S5'!$E$6:$E$20,"Ambos")+SUMIFS('S6'!$I$6:$I$17,'S6'!$B$6:$B$17,$A71,'S6'!$E$6:$E$17,"Víctor")+SUMIFS('S6'!$I$6:$I$17,'S6'!$B$6:$B$17,$A71,'S6'!$E$6:$E$17,"Ambos")+SUMIFS('S7'!$I$6:$I$19,'S7'!$B$6:$B$19,$A71,'S7'!$E$6:$E$19,"Víctor")+SUMIFS('S7'!$I$6:$I$19,'S7'!$B$6:$B$19,$A71,'S7'!$E$6:$E$19,"Ambos")+SUMIFS('S8'!$I$6:$I$23,'S8'!$B$6:$B$23,$A71,'S8'!$E$6:$E$23,"Víctor")+SUMIFS('S8'!$I$6:$I$23,'S8'!$B$6:$B$23,$A71,'S8'!$E$6:$E$23,"Ambos")+SUMIFS('S9'!$I$6:$I$15,'S9'!$B$6:$B$15,$A71,'S9'!$E$6:$E$15,"Víctor")+SUMIFS('S9'!$I$6:$I$15,'S9'!$B$6:$B$15,$A71,'S9'!$E$6:$E$15,"Ambos")+SUMIFS('S10'!$I$6:$I$13,'S10'!$B$6:$B$13,$A71,'S10'!$E$6:$E$13,"Víctor")+SUMIFS('S10'!$I$6:$I$13,'S10'!$B$6:$B$13,$A71,'S10'!$E$6:$E$13,"Ambos")+SUMIFS('Holgura'!$I$6:$I$11,'Holgura'!$B$6:$B$11,$A71,'Holgura'!$E$6:$E$11,"Víctor")+SUMIFS('Holgura'!$I$6:$I$11,'Holgura'!$B$6:$B$11,$A71,'Holgura'!$E$6:$E$11,"Ambos")+SUMIFS('Entrega'!$I$6:$I$9,'Entrega'!$B$6:$B$9,$A71,'Entrega'!$E$6:$E$9,"Víctor")+SUMIFS('Entrega'!$I$6:$I$9,'Entrega'!$B$6:$B$9,$A71,'Entrega'!$E$6:$E$9,"Ambos")+SUMIFS('Defensa'!$I$6:$I$10,'Defensa'!$B$6:$B$10,$A71,'Defensa'!$E$6:$E$10,"Víctor")+SUMIFS('Defensa'!$I$6:$I$10,'Defensa'!$B$6:$B$10,$A71,'Defensa'!$E$6:$E$10,"Ambos")</f>
         <v/>
       </c>
       <c r="E71" s="21">
-        <f>SUMIFS('S1'!$I$6:$I$32,'S1'!$B$6:$B$32,$A71,'S1'!$E$6:$E$32,"Diego")+SUMIFS('S1'!$I$6:$I$32,'S1'!$B$6:$B$32,$A71,'S1'!$E$6:$E$32,"Ambos")+SUMIFS('S2'!$I$6:$I$23,'S2'!$B$6:$B$23,$A71,'S2'!$E$6:$E$23,"Diego")+SUMIFS('S2'!$I$6:$I$23,'S2'!$B$6:$B$23,$A71,'S2'!$E$6:$E$23,"Ambos")+SUMIFS('S3'!$I$6:$I$19,'S3'!$B$6:$B$19,$A71,'S3'!$E$6:$E$19,"Diego")+SUMIFS('S3'!$I$6:$I$19,'S3'!$B$6:$B$19,$A71,'S3'!$E$6:$E$19,"Ambos")+SUMIFS('S4'!$I$6:$I$20,'S4'!$B$6:$B$20,$A71,'S4'!$E$6:$E$20,"Diego")+SUMIFS('S4'!$I$6:$I$20,'S4'!$B$6:$B$20,$A71,'S4'!$E$6:$E$20,"Ambos")+SUMIFS('S5'!$I$6:$I$20,'S5'!$B$6:$B$20,$A71,'S5'!$E$6:$E$20,"Diego")+SUMIFS('S5'!$I$6:$I$20,'S5'!$B$6:$B$20,$A71,'S5'!$E$6:$E$20,"Ambos")+SUMIFS('S6'!$I$6:$I$17,'S6'!$B$6:$B$17,$A71,'S6'!$E$6:$E$17,"Diego")+SUMIFS('S6'!$I$6:$I$17,'S6'!$B$6:$B$17,$A71,'S6'!$E$6:$E$17,"Ambos")+SUMIFS('S7'!$I$6:$I$19,'S7'!$B$6:$B$19,$A71,'S7'!$E$6:$E$19,"Diego")+SUMIFS('S7'!$I$6:$I$19,'S7'!$B$6:$B$19,$A71,'S7'!$E$6:$E$19,"Ambos")+SUMIFS('S8'!$I$6:$I$23,'S8'!$B$6:$B$23,$A71,'S8'!$E$6:$E$23,"Diego")+SUMIFS('S8'!$I$6:$I$23,'S8'!$B$6:$B$23,$A71,'S8'!$E$6:$E$23,"Ambos")+SUMIFS('S9'!$I$6:$I$15,'S9'!$B$6:$B$15,$A71,'S9'!$E$6:$E$15,"Diego")+SUMIFS('S9'!$I$6:$I$15,'S9'!$B$6:$B$15,$A71,'S9'!$E$6:$E$15,"Ambos")+SUMIFS('S10'!$I$6:$I$13,'S10'!$B$6:$B$13,$A71,'S10'!$E$6:$E$13,"Diego")+SUMIFS('S10'!$I$6:$I$13,'S10'!$B$6:$B$13,$A71,'S10'!$E$6:$E$13,"Ambos")+SUMIFS('Holgura'!$I$6:$I$11,'Holgura'!$B$6:$B$11,$A71,'Holgura'!$E$6:$E$11,"Diego")+SUMIFS('Holgura'!$I$6:$I$11,'Holgura'!$B$6:$B$11,$A71,'Holgura'!$E$6:$E$11,"Ambos")+SUMIFS('Entrega'!$I$6:$I$9,'Entrega'!$B$6:$B$9,$A71,'Entrega'!$E$6:$E$9,"Diego")+SUMIFS('Entrega'!$I$6:$I$9,'Entrega'!$B$6:$B$9,$A71,'Entrega'!$E$6:$E$9,"Ambos")+SUMIFS('Defensa'!$I$6:$I$10,'Defensa'!$B$6:$B$10,$A71,'Defensa'!$E$6:$E$10,"Diego")+SUMIFS('Defensa'!$I$6:$I$10,'Defensa'!$B$6:$B$10,$A71,'Defensa'!$E$6:$E$10,"Ambos")</f>
+        <f>SUMIFS('S1'!$I$6:$I$32,'S1'!$B$6:$B$32,$A71,'S1'!$E$6:$E$32,"Diego")+SUMIFS('S1'!$I$6:$I$32,'S1'!$B$6:$B$32,$A71,'S1'!$E$6:$E$32,"Ambos")+SUMIFS('S2'!$I$6:$I$23,'S2'!$B$6:$B$23,$A71,'S2'!$E$6:$E$23,"Diego")+SUMIFS('S2'!$I$6:$I$23,'S2'!$B$6:$B$23,$A71,'S2'!$E$6:$E$23,"Ambos")+SUMIFS('S3'!$I$6:$I$24,'S3'!$B$6:$B$24,$A71,'S3'!$E$6:$E$24,"Diego")+SUMIFS('S3'!$I$6:$I$24,'S3'!$B$6:$B$24,$A71,'S3'!$E$6:$E$24,"Ambos")+SUMIFS('S4'!$I$6:$I$22,'S4'!$B$6:$B$22,$A71,'S4'!$E$6:$E$22,"Diego")+SUMIFS('S4'!$I$6:$I$22,'S4'!$B$6:$B$22,$A71,'S4'!$E$6:$E$22,"Ambos")+SUMIFS('S5'!$I$6:$I$20,'S5'!$B$6:$B$20,$A71,'S5'!$E$6:$E$20,"Diego")+SUMIFS('S5'!$I$6:$I$20,'S5'!$B$6:$B$20,$A71,'S5'!$E$6:$E$20,"Ambos")+SUMIFS('S6'!$I$6:$I$17,'S6'!$B$6:$B$17,$A71,'S6'!$E$6:$E$17,"Diego")+SUMIFS('S6'!$I$6:$I$17,'S6'!$B$6:$B$17,$A71,'S6'!$E$6:$E$17,"Ambos")+SUMIFS('S7'!$I$6:$I$19,'S7'!$B$6:$B$19,$A71,'S7'!$E$6:$E$19,"Diego")+SUMIFS('S7'!$I$6:$I$19,'S7'!$B$6:$B$19,$A71,'S7'!$E$6:$E$19,"Ambos")+SUMIFS('S8'!$I$6:$I$23,'S8'!$B$6:$B$23,$A71,'S8'!$E$6:$E$23,"Diego")+SUMIFS('S8'!$I$6:$I$23,'S8'!$B$6:$B$23,$A71,'S8'!$E$6:$E$23,"Ambos")+SUMIFS('S9'!$I$6:$I$15,'S9'!$B$6:$B$15,$A71,'S9'!$E$6:$E$15,"Diego")+SUMIFS('S9'!$I$6:$I$15,'S9'!$B$6:$B$15,$A71,'S9'!$E$6:$E$15,"Ambos")+SUMIFS('S10'!$I$6:$I$13,'S10'!$B$6:$B$13,$A71,'S10'!$E$6:$E$13,"Diego")+SUMIFS('S10'!$I$6:$I$13,'S10'!$B$6:$B$13,$A71,'S10'!$E$6:$E$13,"Ambos")+SUMIFS('Holgura'!$I$6:$I$11,'Holgura'!$B$6:$B$11,$A71,'Holgura'!$E$6:$E$11,"Diego")+SUMIFS('Holgura'!$I$6:$I$11,'Holgura'!$B$6:$B$11,$A71,'Holgura'!$E$6:$E$11,"Ambos")+SUMIFS('Entrega'!$I$6:$I$9,'Entrega'!$B$6:$B$9,$A71,'Entrega'!$E$6:$E$9,"Diego")+SUMIFS('Entrega'!$I$6:$I$9,'Entrega'!$B$6:$B$9,$A71,'Entrega'!$E$6:$E$9,"Ambos")+SUMIFS('Defensa'!$I$6:$I$10,'Defensa'!$B$6:$B$10,$A71,'Defensa'!$E$6:$E$10,"Diego")+SUMIFS('Defensa'!$I$6:$I$10,'Defensa'!$B$6:$B$10,$A71,'Defensa'!$E$6:$E$10,"Ambos")</f>
         <v/>
       </c>
       <c r="F71" s="21">
-        <f>COUNTIFS('S1'!$B$6:$B$32,$A71,'S1'!$E$6:$E$32,"Víctor")+COUNTIFS('S1'!$B$6:$B$32,$A71,'S1'!$E$6:$E$32,"Ambos")+COUNTIFS('S2'!$B$6:$B$23,$A71,'S2'!$E$6:$E$23,"Víctor")+COUNTIFS('S2'!$B$6:$B$23,$A71,'S2'!$E$6:$E$23,"Ambos")+COUNTIFS('S3'!$B$6:$B$19,$A71,'S3'!$E$6:$E$19,"Víctor")+COUNTIFS('S3'!$B$6:$B$19,$A71,'S3'!$E$6:$E$19,"Ambos")+COUNTIFS('S4'!$B$6:$B$20,$A71,'S4'!$E$6:$E$20,"Víctor")+COUNTIFS('S4'!$B$6:$B$20,$A71,'S4'!$E$6:$E$20,"Ambos")+COUNTIFS('S5'!$B$6:$B$20,$A71,'S5'!$E$6:$E$20,"Víctor")+COUNTIFS('S5'!$B$6:$B$20,$A71,'S5'!$E$6:$E$20,"Ambos")+COUNTIFS('S6'!$B$6:$B$17,$A71,'S6'!$E$6:$E$17,"Víctor")+COUNTIFS('S6'!$B$6:$B$17,$A71,'S6'!$E$6:$E$17,"Ambos")+COUNTIFS('S7'!$B$6:$B$19,$A71,'S7'!$E$6:$E$19,"Víctor")+COUNTIFS('S7'!$B$6:$B$19,$A71,'S7'!$E$6:$E$19,"Ambos")+COUNTIFS('S8'!$B$6:$B$23,$A71,'S8'!$E$6:$E$23,"Víctor")+COUNTIFS('S8'!$B$6:$B$23,$A71,'S8'!$E$6:$E$23,"Ambos")+COUNTIFS('S9'!$B$6:$B$15,$A71,'S9'!$E$6:$E$15,"Víctor")+COUNTIFS('S9'!$B$6:$B$15,$A71,'S9'!$E$6:$E$15,"Ambos")+COUNTIFS('S10'!$B$6:$B$13,$A71,'S10'!$E$6:$E$13,"Víctor")+COUNTIFS('S10'!$B$6:$B$13,$A71,'S10'!$E$6:$E$13,"Ambos")+COUNTIFS('Holgura'!$B$6:$B$11,$A71,'Holgura'!$E$6:$E$11,"Víctor")+COUNTIFS('Holgura'!$B$6:$B$11,$A71,'Holgura'!$E$6:$E$11,"Ambos")+COUNTIFS('Entrega'!$B$6:$B$9,$A71,'Entrega'!$E$6:$E$9,"Víctor")+COUNTIFS('Entrega'!$B$6:$B$9,$A71,'Entrega'!$E$6:$E$9,"Ambos")+COUNTIFS('Defensa'!$B$6:$B$10,$A71,'Defensa'!$E$6:$E$10,"Víctor")+COUNTIFS('Defensa'!$B$6:$B$10,$A71,'Defensa'!$E$6:$E$10,"Ambos")</f>
+        <f>COUNTIFS('S1'!$B$6:$B$32,$A71,'S1'!$E$6:$E$32,"Víctor")+COUNTIFS('S1'!$B$6:$B$32,$A71,'S1'!$E$6:$E$32,"Ambos")+COUNTIFS('S2'!$B$6:$B$23,$A71,'S2'!$E$6:$E$23,"Víctor")+COUNTIFS('S2'!$B$6:$B$23,$A71,'S2'!$E$6:$E$23,"Ambos")+COUNTIFS('S3'!$B$6:$B$24,$A71,'S3'!$E$6:$E$24,"Víctor")+COUNTIFS('S3'!$B$6:$B$24,$A71,'S3'!$E$6:$E$24,"Ambos")+COUNTIFS('S4'!$B$6:$B$22,$A71,'S4'!$E$6:$E$22,"Víctor")+COUNTIFS('S4'!$B$6:$B$22,$A71,'S4'!$E$6:$E$22,"Ambos")+COUNTIFS('S5'!$B$6:$B$20,$A71,'S5'!$E$6:$E$20,"Víctor")+COUNTIFS('S5'!$B$6:$B$20,$A71,'S5'!$E$6:$E$20,"Ambos")+COUNTIFS('S6'!$B$6:$B$17,$A71,'S6'!$E$6:$E$17,"Víctor")+COUNTIFS('S6'!$B$6:$B$17,$A71,'S6'!$E$6:$E$17,"Ambos")+COUNTIFS('S7'!$B$6:$B$19,$A71,'S7'!$E$6:$E$19,"Víctor")+COUNTIFS('S7'!$B$6:$B$19,$A71,'S7'!$E$6:$E$19,"Ambos")+COUNTIFS('S8'!$B$6:$B$23,$A71,'S8'!$E$6:$E$23,"Víctor")+COUNTIFS('S8'!$B$6:$B$23,$A71,'S8'!$E$6:$E$23,"Ambos")+COUNTIFS('S9'!$B$6:$B$15,$A71,'S9'!$E$6:$E$15,"Víctor")+COUNTIFS('S9'!$B$6:$B$15,$A71,'S9'!$E$6:$E$15,"Ambos")+COUNTIFS('S10'!$B$6:$B$13,$A71,'S10'!$E$6:$E$13,"Víctor")+COUNTIFS('S10'!$B$6:$B$13,$A71,'S10'!$E$6:$E$13,"Ambos")+COUNTIFS('Holgura'!$B$6:$B$11,$A71,'Holgura'!$E$6:$E$11,"Víctor")+COUNTIFS('Holgura'!$B$6:$B$11,$A71,'Holgura'!$E$6:$E$11,"Ambos")+COUNTIFS('Entrega'!$B$6:$B$9,$A71,'Entrega'!$E$6:$E$9,"Víctor")+COUNTIFS('Entrega'!$B$6:$B$9,$A71,'Entrega'!$E$6:$E$9,"Ambos")+COUNTIFS('Defensa'!$B$6:$B$10,$A71,'Defensa'!$E$6:$E$10,"Víctor")+COUNTIFS('Defensa'!$B$6:$B$10,$A71,'Defensa'!$E$6:$E$10,"Ambos")</f>
         <v/>
       </c>
       <c r="G71" s="21">
-        <f>COUNTIFS('S1'!$B$6:$B$32,$A71,'S1'!$E$6:$E$32,"Diego")+COUNTIFS('S1'!$B$6:$B$32,$A71,'S1'!$E$6:$E$32,"Ambos")+COUNTIFS('S2'!$B$6:$B$23,$A71,'S2'!$E$6:$E$23,"Diego")+COUNTIFS('S2'!$B$6:$B$23,$A71,'S2'!$E$6:$E$23,"Ambos")+COUNTIFS('S3'!$B$6:$B$19,$A71,'S3'!$E$6:$E$19,"Diego")+COUNTIFS('S3'!$B$6:$B$19,$A71,'S3'!$E$6:$E$19,"Ambos")+COUNTIFS('S4'!$B$6:$B$20,$A71,'S4'!$E$6:$E$20,"Diego")+COUNTIFS('S4'!$B$6:$B$20,$A71,'S4'!$E$6:$E$20,"Ambos")+COUNTIFS('S5'!$B$6:$B$20,$A71,'S5'!$E$6:$E$20,"Diego")+COUNTIFS('S5'!$B$6:$B$20,$A71,'S5'!$E$6:$E$20,"Ambos")+COUNTIFS('S6'!$B$6:$B$17,$A71,'S6'!$E$6:$E$17,"Diego")+COUNTIFS('S6'!$B$6:$B$17,$A71,'S6'!$E$6:$E$17,"Ambos")+COUNTIFS('S7'!$B$6:$B$19,$A71,'S7'!$E$6:$E$19,"Diego")+COUNTIFS('S7'!$B$6:$B$19,$A71,'S7'!$E$6:$E$19,"Ambos")+COUNTIFS('S8'!$B$6:$B$23,$A71,'S8'!$E$6:$E$23,"Diego")+COUNTIFS('S8'!$B$6:$B$23,$A71,'S8'!$E$6:$E$23,"Ambos")+COUNTIFS('S9'!$B$6:$B$15,$A71,'S9'!$E$6:$E$15,"Diego")+COUNTIFS('S9'!$B$6:$B$15,$A71,'S9'!$E$6:$E$15,"Ambos")+COUNTIFS('S10'!$B$6:$B$13,$A71,'S10'!$E$6:$E$13,"Diego")+COUNTIFS('S10'!$B$6:$B$13,$A71,'S10'!$E$6:$E$13,"Ambos")+COUNTIFS('Holgura'!$B$6:$B$11,$A71,'Holgura'!$E$6:$E$11,"Diego")+COUNTIFS('Holgura'!$B$6:$B$11,$A71,'Holgura'!$E$6:$E$11,"Ambos")+COUNTIFS('Entrega'!$B$6:$B$9,$A71,'Entrega'!$E$6:$E$9,"Diego")+COUNTIFS('Entrega'!$B$6:$B$9,$A71,'Entrega'!$E$6:$E$9,"Ambos")+COUNTIFS('Defensa'!$B$6:$B$10,$A71,'Defensa'!$E$6:$E$10,"Diego")+COUNTIFS('Defensa'!$B$6:$B$10,$A71,'Defensa'!$E$6:$E$10,"Ambos")</f>
+        <f>COUNTIFS('S1'!$B$6:$B$32,$A71,'S1'!$E$6:$E$32,"Diego")+COUNTIFS('S1'!$B$6:$B$32,$A71,'S1'!$E$6:$E$32,"Ambos")+COUNTIFS('S2'!$B$6:$B$23,$A71,'S2'!$E$6:$E$23,"Diego")+COUNTIFS('S2'!$B$6:$B$23,$A71,'S2'!$E$6:$E$23,"Ambos")+COUNTIFS('S3'!$B$6:$B$24,$A71,'S3'!$E$6:$E$24,"Diego")+COUNTIFS('S3'!$B$6:$B$24,$A71,'S3'!$E$6:$E$24,"Ambos")+COUNTIFS('S4'!$B$6:$B$22,$A71,'S4'!$E$6:$E$22,"Diego")+COUNTIFS('S4'!$B$6:$B$22,$A71,'S4'!$E$6:$E$22,"Ambos")+COUNTIFS('S5'!$B$6:$B$20,$A71,'S5'!$E$6:$E$20,"Diego")+COUNTIFS('S5'!$B$6:$B$20,$A71,'S5'!$E$6:$E$20,"Ambos")+COUNTIFS('S6'!$B$6:$B$17,$A71,'S6'!$E$6:$E$17,"Diego")+COUNTIFS('S6'!$B$6:$B$17,$A71,'S6'!$E$6:$E$17,"Ambos")+COUNTIFS('S7'!$B$6:$B$19,$A71,'S7'!$E$6:$E$19,"Diego")+COUNTIFS('S7'!$B$6:$B$19,$A71,'S7'!$E$6:$E$19,"Ambos")+COUNTIFS('S8'!$B$6:$B$23,$A71,'S8'!$E$6:$E$23,"Diego")+COUNTIFS('S8'!$B$6:$B$23,$A71,'S8'!$E$6:$E$23,"Ambos")+COUNTIFS('S9'!$B$6:$B$15,$A71,'S9'!$E$6:$E$15,"Diego")+COUNTIFS('S9'!$B$6:$B$15,$A71,'S9'!$E$6:$E$15,"Ambos")+COUNTIFS('S10'!$B$6:$B$13,$A71,'S10'!$E$6:$E$13,"Diego")+COUNTIFS('S10'!$B$6:$B$13,$A71,'S10'!$E$6:$E$13,"Ambos")+COUNTIFS('Holgura'!$B$6:$B$11,$A71,'Holgura'!$E$6:$E$11,"Diego")+COUNTIFS('Holgura'!$B$6:$B$11,$A71,'Holgura'!$E$6:$E$11,"Ambos")+COUNTIFS('Entrega'!$B$6:$B$9,$A71,'Entrega'!$E$6:$E$9,"Diego")+COUNTIFS('Entrega'!$B$6:$B$9,$A71,'Entrega'!$E$6:$E$9,"Ambos")+COUNTIFS('Defensa'!$B$6:$B$10,$A71,'Defensa'!$E$6:$E$10,"Diego")+COUNTIFS('Defensa'!$B$6:$B$10,$A71,'Defensa'!$E$6:$E$10,"Ambos")</f>
         <v/>
       </c>
     </row>
@@ -10623,19 +10644,19 @@
         <v/>
       </c>
       <c r="D72" s="21">
-        <f>SUMIFS('S1'!$I$6:$I$32,'S1'!$B$6:$B$32,$A72,'S1'!$E$6:$E$32,"Víctor")+SUMIFS('S1'!$I$6:$I$32,'S1'!$B$6:$B$32,$A72,'S1'!$E$6:$E$32,"Ambos")+SUMIFS('S2'!$I$6:$I$23,'S2'!$B$6:$B$23,$A72,'S2'!$E$6:$E$23,"Víctor")+SUMIFS('S2'!$I$6:$I$23,'S2'!$B$6:$B$23,$A72,'S2'!$E$6:$E$23,"Ambos")+SUMIFS('S3'!$I$6:$I$19,'S3'!$B$6:$B$19,$A72,'S3'!$E$6:$E$19,"Víctor")+SUMIFS('S3'!$I$6:$I$19,'S3'!$B$6:$B$19,$A72,'S3'!$E$6:$E$19,"Ambos")+SUMIFS('S4'!$I$6:$I$20,'S4'!$B$6:$B$20,$A72,'S4'!$E$6:$E$20,"Víctor")+SUMIFS('S4'!$I$6:$I$20,'S4'!$B$6:$B$20,$A72,'S4'!$E$6:$E$20,"Ambos")+SUMIFS('S5'!$I$6:$I$20,'S5'!$B$6:$B$20,$A72,'S5'!$E$6:$E$20,"Víctor")+SUMIFS('S5'!$I$6:$I$20,'S5'!$B$6:$B$20,$A72,'S5'!$E$6:$E$20,"Ambos")+SUMIFS('S6'!$I$6:$I$17,'S6'!$B$6:$B$17,$A72,'S6'!$E$6:$E$17,"Víctor")+SUMIFS('S6'!$I$6:$I$17,'S6'!$B$6:$B$17,$A72,'S6'!$E$6:$E$17,"Ambos")+SUMIFS('S7'!$I$6:$I$19,'S7'!$B$6:$B$19,$A72,'S7'!$E$6:$E$19,"Víctor")+SUMIFS('S7'!$I$6:$I$19,'S7'!$B$6:$B$19,$A72,'S7'!$E$6:$E$19,"Ambos")+SUMIFS('S8'!$I$6:$I$23,'S8'!$B$6:$B$23,$A72,'S8'!$E$6:$E$23,"Víctor")+SUMIFS('S8'!$I$6:$I$23,'S8'!$B$6:$B$23,$A72,'S8'!$E$6:$E$23,"Ambos")+SUMIFS('S9'!$I$6:$I$15,'S9'!$B$6:$B$15,$A72,'S9'!$E$6:$E$15,"Víctor")+SUMIFS('S9'!$I$6:$I$15,'S9'!$B$6:$B$15,$A72,'S9'!$E$6:$E$15,"Ambos")+SUMIFS('S10'!$I$6:$I$13,'S10'!$B$6:$B$13,$A72,'S10'!$E$6:$E$13,"Víctor")+SUMIFS('S10'!$I$6:$I$13,'S10'!$B$6:$B$13,$A72,'S10'!$E$6:$E$13,"Ambos")+SUMIFS('Holgura'!$I$6:$I$11,'Holgura'!$B$6:$B$11,$A72,'Holgura'!$E$6:$E$11,"Víctor")+SUMIFS('Holgura'!$I$6:$I$11,'Holgura'!$B$6:$B$11,$A72,'Holgura'!$E$6:$E$11,"Ambos")+SUMIFS('Entrega'!$I$6:$I$9,'Entrega'!$B$6:$B$9,$A72,'Entrega'!$E$6:$E$9,"Víctor")+SUMIFS('Entrega'!$I$6:$I$9,'Entrega'!$B$6:$B$9,$A72,'Entrega'!$E$6:$E$9,"Ambos")+SUMIFS('Defensa'!$I$6:$I$10,'Defensa'!$B$6:$B$10,$A72,'Defensa'!$E$6:$E$10,"Víctor")+SUMIFS('Defensa'!$I$6:$I$10,'Defensa'!$B$6:$B$10,$A72,'Defensa'!$E$6:$E$10,"Ambos")</f>
+        <f>SUMIFS('S1'!$I$6:$I$32,'S1'!$B$6:$B$32,$A72,'S1'!$E$6:$E$32,"Víctor")+SUMIFS('S1'!$I$6:$I$32,'S1'!$B$6:$B$32,$A72,'S1'!$E$6:$E$32,"Ambos")+SUMIFS('S2'!$I$6:$I$23,'S2'!$B$6:$B$23,$A72,'S2'!$E$6:$E$23,"Víctor")+SUMIFS('S2'!$I$6:$I$23,'S2'!$B$6:$B$23,$A72,'S2'!$E$6:$E$23,"Ambos")+SUMIFS('S3'!$I$6:$I$24,'S3'!$B$6:$B$24,$A72,'S3'!$E$6:$E$24,"Víctor")+SUMIFS('S3'!$I$6:$I$24,'S3'!$B$6:$B$24,$A72,'S3'!$E$6:$E$24,"Ambos")+SUMIFS('S4'!$I$6:$I$22,'S4'!$B$6:$B$22,$A72,'S4'!$E$6:$E$22,"Víctor")+SUMIFS('S4'!$I$6:$I$22,'S4'!$B$6:$B$22,$A72,'S4'!$E$6:$E$22,"Ambos")+SUMIFS('S5'!$I$6:$I$20,'S5'!$B$6:$B$20,$A72,'S5'!$E$6:$E$20,"Víctor")+SUMIFS('S5'!$I$6:$I$20,'S5'!$B$6:$B$20,$A72,'S5'!$E$6:$E$20,"Ambos")+SUMIFS('S6'!$I$6:$I$17,'S6'!$B$6:$B$17,$A72,'S6'!$E$6:$E$17,"Víctor")+SUMIFS('S6'!$I$6:$I$17,'S6'!$B$6:$B$17,$A72,'S6'!$E$6:$E$17,"Ambos")+SUMIFS('S7'!$I$6:$I$19,'S7'!$B$6:$B$19,$A72,'S7'!$E$6:$E$19,"Víctor")+SUMIFS('S7'!$I$6:$I$19,'S7'!$B$6:$B$19,$A72,'S7'!$E$6:$E$19,"Ambos")+SUMIFS('S8'!$I$6:$I$23,'S8'!$B$6:$B$23,$A72,'S8'!$E$6:$E$23,"Víctor")+SUMIFS('S8'!$I$6:$I$23,'S8'!$B$6:$B$23,$A72,'S8'!$E$6:$E$23,"Ambos")+SUMIFS('S9'!$I$6:$I$15,'S9'!$B$6:$B$15,$A72,'S9'!$E$6:$E$15,"Víctor")+SUMIFS('S9'!$I$6:$I$15,'S9'!$B$6:$B$15,$A72,'S9'!$E$6:$E$15,"Ambos")+SUMIFS('S10'!$I$6:$I$13,'S10'!$B$6:$B$13,$A72,'S10'!$E$6:$E$13,"Víctor")+SUMIFS('S10'!$I$6:$I$13,'S10'!$B$6:$B$13,$A72,'S10'!$E$6:$E$13,"Ambos")+SUMIFS('Holgura'!$I$6:$I$11,'Holgura'!$B$6:$B$11,$A72,'Holgura'!$E$6:$E$11,"Víctor")+SUMIFS('Holgura'!$I$6:$I$11,'Holgura'!$B$6:$B$11,$A72,'Holgura'!$E$6:$E$11,"Ambos")+SUMIFS('Entrega'!$I$6:$I$9,'Entrega'!$B$6:$B$9,$A72,'Entrega'!$E$6:$E$9,"Víctor")+SUMIFS('Entrega'!$I$6:$I$9,'Entrega'!$B$6:$B$9,$A72,'Entrega'!$E$6:$E$9,"Ambos")+SUMIFS('Defensa'!$I$6:$I$10,'Defensa'!$B$6:$B$10,$A72,'Defensa'!$E$6:$E$10,"Víctor")+SUMIFS('Defensa'!$I$6:$I$10,'Defensa'!$B$6:$B$10,$A72,'Defensa'!$E$6:$E$10,"Ambos")</f>
         <v/>
       </c>
       <c r="E72" s="21">
-        <f>SUMIFS('S1'!$I$6:$I$32,'S1'!$B$6:$B$32,$A72,'S1'!$E$6:$E$32,"Diego")+SUMIFS('S1'!$I$6:$I$32,'S1'!$B$6:$B$32,$A72,'S1'!$E$6:$E$32,"Ambos")+SUMIFS('S2'!$I$6:$I$23,'S2'!$B$6:$B$23,$A72,'S2'!$E$6:$E$23,"Diego")+SUMIFS('S2'!$I$6:$I$23,'S2'!$B$6:$B$23,$A72,'S2'!$E$6:$E$23,"Ambos")+SUMIFS('S3'!$I$6:$I$19,'S3'!$B$6:$B$19,$A72,'S3'!$E$6:$E$19,"Diego")+SUMIFS('S3'!$I$6:$I$19,'S3'!$B$6:$B$19,$A72,'S3'!$E$6:$E$19,"Ambos")+SUMIFS('S4'!$I$6:$I$20,'S4'!$B$6:$B$20,$A72,'S4'!$E$6:$E$20,"Diego")+SUMIFS('S4'!$I$6:$I$20,'S4'!$B$6:$B$20,$A72,'S4'!$E$6:$E$20,"Ambos")+SUMIFS('S5'!$I$6:$I$20,'S5'!$B$6:$B$20,$A72,'S5'!$E$6:$E$20,"Diego")+SUMIFS('S5'!$I$6:$I$20,'S5'!$B$6:$B$20,$A72,'S5'!$E$6:$E$20,"Ambos")+SUMIFS('S6'!$I$6:$I$17,'S6'!$B$6:$B$17,$A72,'S6'!$E$6:$E$17,"Diego")+SUMIFS('S6'!$I$6:$I$17,'S6'!$B$6:$B$17,$A72,'S6'!$E$6:$E$17,"Ambos")+SUMIFS('S7'!$I$6:$I$19,'S7'!$B$6:$B$19,$A72,'S7'!$E$6:$E$19,"Diego")+SUMIFS('S7'!$I$6:$I$19,'S7'!$B$6:$B$19,$A72,'S7'!$E$6:$E$19,"Ambos")+SUMIFS('S8'!$I$6:$I$23,'S8'!$B$6:$B$23,$A72,'S8'!$E$6:$E$23,"Diego")+SUMIFS('S8'!$I$6:$I$23,'S8'!$B$6:$B$23,$A72,'S8'!$E$6:$E$23,"Ambos")+SUMIFS('S9'!$I$6:$I$15,'S9'!$B$6:$B$15,$A72,'S9'!$E$6:$E$15,"Diego")+SUMIFS('S9'!$I$6:$I$15,'S9'!$B$6:$B$15,$A72,'S9'!$E$6:$E$15,"Ambos")+SUMIFS('S10'!$I$6:$I$13,'S10'!$B$6:$B$13,$A72,'S10'!$E$6:$E$13,"Diego")+SUMIFS('S10'!$I$6:$I$13,'S10'!$B$6:$B$13,$A72,'S10'!$E$6:$E$13,"Ambos")+SUMIFS('Holgura'!$I$6:$I$11,'Holgura'!$B$6:$B$11,$A72,'Holgura'!$E$6:$E$11,"Diego")+SUMIFS('Holgura'!$I$6:$I$11,'Holgura'!$B$6:$B$11,$A72,'Holgura'!$E$6:$E$11,"Ambos")+SUMIFS('Entrega'!$I$6:$I$9,'Entrega'!$B$6:$B$9,$A72,'Entrega'!$E$6:$E$9,"Diego")+SUMIFS('Entrega'!$I$6:$I$9,'Entrega'!$B$6:$B$9,$A72,'Entrega'!$E$6:$E$9,"Ambos")+SUMIFS('Defensa'!$I$6:$I$10,'Defensa'!$B$6:$B$10,$A72,'Defensa'!$E$6:$E$10,"Diego")+SUMIFS('Defensa'!$I$6:$I$10,'Defensa'!$B$6:$B$10,$A72,'Defensa'!$E$6:$E$10,"Ambos")</f>
+        <f>SUMIFS('S1'!$I$6:$I$32,'S1'!$B$6:$B$32,$A72,'S1'!$E$6:$E$32,"Diego")+SUMIFS('S1'!$I$6:$I$32,'S1'!$B$6:$B$32,$A72,'S1'!$E$6:$E$32,"Ambos")+SUMIFS('S2'!$I$6:$I$23,'S2'!$B$6:$B$23,$A72,'S2'!$E$6:$E$23,"Diego")+SUMIFS('S2'!$I$6:$I$23,'S2'!$B$6:$B$23,$A72,'S2'!$E$6:$E$23,"Ambos")+SUMIFS('S3'!$I$6:$I$24,'S3'!$B$6:$B$24,$A72,'S3'!$E$6:$E$24,"Diego")+SUMIFS('S3'!$I$6:$I$24,'S3'!$B$6:$B$24,$A72,'S3'!$E$6:$E$24,"Ambos")+SUMIFS('S4'!$I$6:$I$22,'S4'!$B$6:$B$22,$A72,'S4'!$E$6:$E$22,"Diego")+SUMIFS('S4'!$I$6:$I$22,'S4'!$B$6:$B$22,$A72,'S4'!$E$6:$E$22,"Ambos")+SUMIFS('S5'!$I$6:$I$20,'S5'!$B$6:$B$20,$A72,'S5'!$E$6:$E$20,"Diego")+SUMIFS('S5'!$I$6:$I$20,'S5'!$B$6:$B$20,$A72,'S5'!$E$6:$E$20,"Ambos")+SUMIFS('S6'!$I$6:$I$17,'S6'!$B$6:$B$17,$A72,'S6'!$E$6:$E$17,"Diego")+SUMIFS('S6'!$I$6:$I$17,'S6'!$B$6:$B$17,$A72,'S6'!$E$6:$E$17,"Ambos")+SUMIFS('S7'!$I$6:$I$19,'S7'!$B$6:$B$19,$A72,'S7'!$E$6:$E$19,"Diego")+SUMIFS('S7'!$I$6:$I$19,'S7'!$B$6:$B$19,$A72,'S7'!$E$6:$E$19,"Ambos")+SUMIFS('S8'!$I$6:$I$23,'S8'!$B$6:$B$23,$A72,'S8'!$E$6:$E$23,"Diego")+SUMIFS('S8'!$I$6:$I$23,'S8'!$B$6:$B$23,$A72,'S8'!$E$6:$E$23,"Ambos")+SUMIFS('S9'!$I$6:$I$15,'S9'!$B$6:$B$15,$A72,'S9'!$E$6:$E$15,"Diego")+SUMIFS('S9'!$I$6:$I$15,'S9'!$B$6:$B$15,$A72,'S9'!$E$6:$E$15,"Ambos")+SUMIFS('S10'!$I$6:$I$13,'S10'!$B$6:$B$13,$A72,'S10'!$E$6:$E$13,"Diego")+SUMIFS('S10'!$I$6:$I$13,'S10'!$B$6:$B$13,$A72,'S10'!$E$6:$E$13,"Ambos")+SUMIFS('Holgura'!$I$6:$I$11,'Holgura'!$B$6:$B$11,$A72,'Holgura'!$E$6:$E$11,"Diego")+SUMIFS('Holgura'!$I$6:$I$11,'Holgura'!$B$6:$B$11,$A72,'Holgura'!$E$6:$E$11,"Ambos")+SUMIFS('Entrega'!$I$6:$I$9,'Entrega'!$B$6:$B$9,$A72,'Entrega'!$E$6:$E$9,"Diego")+SUMIFS('Entrega'!$I$6:$I$9,'Entrega'!$B$6:$B$9,$A72,'Entrega'!$E$6:$E$9,"Ambos")+SUMIFS('Defensa'!$I$6:$I$10,'Defensa'!$B$6:$B$10,$A72,'Defensa'!$E$6:$E$10,"Diego")+SUMIFS('Defensa'!$I$6:$I$10,'Defensa'!$B$6:$B$10,$A72,'Defensa'!$E$6:$E$10,"Ambos")</f>
         <v/>
       </c>
       <c r="F72" s="21">
-        <f>COUNTIFS('S1'!$B$6:$B$32,$A72,'S1'!$E$6:$E$32,"Víctor")+COUNTIFS('S1'!$B$6:$B$32,$A72,'S1'!$E$6:$E$32,"Ambos")+COUNTIFS('S2'!$B$6:$B$23,$A72,'S2'!$E$6:$E$23,"Víctor")+COUNTIFS('S2'!$B$6:$B$23,$A72,'S2'!$E$6:$E$23,"Ambos")+COUNTIFS('S3'!$B$6:$B$19,$A72,'S3'!$E$6:$E$19,"Víctor")+COUNTIFS('S3'!$B$6:$B$19,$A72,'S3'!$E$6:$E$19,"Ambos")+COUNTIFS('S4'!$B$6:$B$20,$A72,'S4'!$E$6:$E$20,"Víctor")+COUNTIFS('S4'!$B$6:$B$20,$A72,'S4'!$E$6:$E$20,"Ambos")+COUNTIFS('S5'!$B$6:$B$20,$A72,'S5'!$E$6:$E$20,"Víctor")+COUNTIFS('S5'!$B$6:$B$20,$A72,'S5'!$E$6:$E$20,"Ambos")+COUNTIFS('S6'!$B$6:$B$17,$A72,'S6'!$E$6:$E$17,"Víctor")+COUNTIFS('S6'!$B$6:$B$17,$A72,'S6'!$E$6:$E$17,"Ambos")+COUNTIFS('S7'!$B$6:$B$19,$A72,'S7'!$E$6:$E$19,"Víctor")+COUNTIFS('S7'!$B$6:$B$19,$A72,'S7'!$E$6:$E$19,"Ambos")+COUNTIFS('S8'!$B$6:$B$23,$A72,'S8'!$E$6:$E$23,"Víctor")+COUNTIFS('S8'!$B$6:$B$23,$A72,'S8'!$E$6:$E$23,"Ambos")+COUNTIFS('S9'!$B$6:$B$15,$A72,'S9'!$E$6:$E$15,"Víctor")+COUNTIFS('S9'!$B$6:$B$15,$A72,'S9'!$E$6:$E$15,"Ambos")+COUNTIFS('S10'!$B$6:$B$13,$A72,'S10'!$E$6:$E$13,"Víctor")+COUNTIFS('S10'!$B$6:$B$13,$A72,'S10'!$E$6:$E$13,"Ambos")+COUNTIFS('Holgura'!$B$6:$B$11,$A72,'Holgura'!$E$6:$E$11,"Víctor")+COUNTIFS('Holgura'!$B$6:$B$11,$A72,'Holgura'!$E$6:$E$11,"Ambos")+COUNTIFS('Entrega'!$B$6:$B$9,$A72,'Entrega'!$E$6:$E$9,"Víctor")+COUNTIFS('Entrega'!$B$6:$B$9,$A72,'Entrega'!$E$6:$E$9,"Ambos")+COUNTIFS('Defensa'!$B$6:$B$10,$A72,'Defensa'!$E$6:$E$10,"Víctor")+COUNTIFS('Defensa'!$B$6:$B$10,$A72,'Defensa'!$E$6:$E$10,"Ambos")</f>
+        <f>COUNTIFS('S1'!$B$6:$B$32,$A72,'S1'!$E$6:$E$32,"Víctor")+COUNTIFS('S1'!$B$6:$B$32,$A72,'S1'!$E$6:$E$32,"Ambos")+COUNTIFS('S2'!$B$6:$B$23,$A72,'S2'!$E$6:$E$23,"Víctor")+COUNTIFS('S2'!$B$6:$B$23,$A72,'S2'!$E$6:$E$23,"Ambos")+COUNTIFS('S3'!$B$6:$B$24,$A72,'S3'!$E$6:$E$24,"Víctor")+COUNTIFS('S3'!$B$6:$B$24,$A72,'S3'!$E$6:$E$24,"Ambos")+COUNTIFS('S4'!$B$6:$B$22,$A72,'S4'!$E$6:$E$22,"Víctor")+COUNTIFS('S4'!$B$6:$B$22,$A72,'S4'!$E$6:$E$22,"Ambos")+COUNTIFS('S5'!$B$6:$B$20,$A72,'S5'!$E$6:$E$20,"Víctor")+COUNTIFS('S5'!$B$6:$B$20,$A72,'S5'!$E$6:$E$20,"Ambos")+COUNTIFS('S6'!$B$6:$B$17,$A72,'S6'!$E$6:$E$17,"Víctor")+COUNTIFS('S6'!$B$6:$B$17,$A72,'S6'!$E$6:$E$17,"Ambos")+COUNTIFS('S7'!$B$6:$B$19,$A72,'S7'!$E$6:$E$19,"Víctor")+COUNTIFS('S7'!$B$6:$B$19,$A72,'S7'!$E$6:$E$19,"Ambos")+COUNTIFS('S8'!$B$6:$B$23,$A72,'S8'!$E$6:$E$23,"Víctor")+COUNTIFS('S8'!$B$6:$B$23,$A72,'S8'!$E$6:$E$23,"Ambos")+COUNTIFS('S9'!$B$6:$B$15,$A72,'S9'!$E$6:$E$15,"Víctor")+COUNTIFS('S9'!$B$6:$B$15,$A72,'S9'!$E$6:$E$15,"Ambos")+COUNTIFS('S10'!$B$6:$B$13,$A72,'S10'!$E$6:$E$13,"Víctor")+COUNTIFS('S10'!$B$6:$B$13,$A72,'S10'!$E$6:$E$13,"Ambos")+COUNTIFS('Holgura'!$B$6:$B$11,$A72,'Holgura'!$E$6:$E$11,"Víctor")+COUNTIFS('Holgura'!$B$6:$B$11,$A72,'Holgura'!$E$6:$E$11,"Ambos")+COUNTIFS('Entrega'!$B$6:$B$9,$A72,'Entrega'!$E$6:$E$9,"Víctor")+COUNTIFS('Entrega'!$B$6:$B$9,$A72,'Entrega'!$E$6:$E$9,"Ambos")+COUNTIFS('Defensa'!$B$6:$B$10,$A72,'Defensa'!$E$6:$E$10,"Víctor")+COUNTIFS('Defensa'!$B$6:$B$10,$A72,'Defensa'!$E$6:$E$10,"Ambos")</f>
         <v/>
       </c>
       <c r="G72" s="21">
-        <f>COUNTIFS('S1'!$B$6:$B$32,$A72,'S1'!$E$6:$E$32,"Diego")+COUNTIFS('S1'!$B$6:$B$32,$A72,'S1'!$E$6:$E$32,"Ambos")+COUNTIFS('S2'!$B$6:$B$23,$A72,'S2'!$E$6:$E$23,"Diego")+COUNTIFS('S2'!$B$6:$B$23,$A72,'S2'!$E$6:$E$23,"Ambos")+COUNTIFS('S3'!$B$6:$B$19,$A72,'S3'!$E$6:$E$19,"Diego")+COUNTIFS('S3'!$B$6:$B$19,$A72,'S3'!$E$6:$E$19,"Ambos")+COUNTIFS('S4'!$B$6:$B$20,$A72,'S4'!$E$6:$E$20,"Diego")+COUNTIFS('S4'!$B$6:$B$20,$A72,'S4'!$E$6:$E$20,"Ambos")+COUNTIFS('S5'!$B$6:$B$20,$A72,'S5'!$E$6:$E$20,"Diego")+COUNTIFS('S5'!$B$6:$B$20,$A72,'S5'!$E$6:$E$20,"Ambos")+COUNTIFS('S6'!$B$6:$B$17,$A72,'S6'!$E$6:$E$17,"Diego")+COUNTIFS('S6'!$B$6:$B$17,$A72,'S6'!$E$6:$E$17,"Ambos")+COUNTIFS('S7'!$B$6:$B$19,$A72,'S7'!$E$6:$E$19,"Diego")+COUNTIFS('S7'!$B$6:$B$19,$A72,'S7'!$E$6:$E$19,"Ambos")+COUNTIFS('S8'!$B$6:$B$23,$A72,'S8'!$E$6:$E$23,"Diego")+COUNTIFS('S8'!$B$6:$B$23,$A72,'S8'!$E$6:$E$23,"Ambos")+COUNTIFS('S9'!$B$6:$B$15,$A72,'S9'!$E$6:$E$15,"Diego")+COUNTIFS('S9'!$B$6:$B$15,$A72,'S9'!$E$6:$E$15,"Ambos")+COUNTIFS('S10'!$B$6:$B$13,$A72,'S10'!$E$6:$E$13,"Diego")+COUNTIFS('S10'!$B$6:$B$13,$A72,'S10'!$E$6:$E$13,"Ambos")+COUNTIFS('Holgura'!$B$6:$B$11,$A72,'Holgura'!$E$6:$E$11,"Diego")+COUNTIFS('Holgura'!$B$6:$B$11,$A72,'Holgura'!$E$6:$E$11,"Ambos")+COUNTIFS('Entrega'!$B$6:$B$9,$A72,'Entrega'!$E$6:$E$9,"Diego")+COUNTIFS('Entrega'!$B$6:$B$9,$A72,'Entrega'!$E$6:$E$9,"Ambos")+COUNTIFS('Defensa'!$B$6:$B$10,$A72,'Defensa'!$E$6:$E$10,"Diego")+COUNTIFS('Defensa'!$B$6:$B$10,$A72,'Defensa'!$E$6:$E$10,"Ambos")</f>
+        <f>COUNTIFS('S1'!$B$6:$B$32,$A72,'S1'!$E$6:$E$32,"Diego")+COUNTIFS('S1'!$B$6:$B$32,$A72,'S1'!$E$6:$E$32,"Ambos")+COUNTIFS('S2'!$B$6:$B$23,$A72,'S2'!$E$6:$E$23,"Diego")+COUNTIFS('S2'!$B$6:$B$23,$A72,'S2'!$E$6:$E$23,"Ambos")+COUNTIFS('S3'!$B$6:$B$24,$A72,'S3'!$E$6:$E$24,"Diego")+COUNTIFS('S3'!$B$6:$B$24,$A72,'S3'!$E$6:$E$24,"Ambos")+COUNTIFS('S4'!$B$6:$B$22,$A72,'S4'!$E$6:$E$22,"Diego")+COUNTIFS('S4'!$B$6:$B$22,$A72,'S4'!$E$6:$E$22,"Ambos")+COUNTIFS('S5'!$B$6:$B$20,$A72,'S5'!$E$6:$E$20,"Diego")+COUNTIFS('S5'!$B$6:$B$20,$A72,'S5'!$E$6:$E$20,"Ambos")+COUNTIFS('S6'!$B$6:$B$17,$A72,'S6'!$E$6:$E$17,"Diego")+COUNTIFS('S6'!$B$6:$B$17,$A72,'S6'!$E$6:$E$17,"Ambos")+COUNTIFS('S7'!$B$6:$B$19,$A72,'S7'!$E$6:$E$19,"Diego")+COUNTIFS('S7'!$B$6:$B$19,$A72,'S7'!$E$6:$E$19,"Ambos")+COUNTIFS('S8'!$B$6:$B$23,$A72,'S8'!$E$6:$E$23,"Diego")+COUNTIFS('S8'!$B$6:$B$23,$A72,'S8'!$E$6:$E$23,"Ambos")+COUNTIFS('S9'!$B$6:$B$15,$A72,'S9'!$E$6:$E$15,"Diego")+COUNTIFS('S9'!$B$6:$B$15,$A72,'S9'!$E$6:$E$15,"Ambos")+COUNTIFS('S10'!$B$6:$B$13,$A72,'S10'!$E$6:$E$13,"Diego")+COUNTIFS('S10'!$B$6:$B$13,$A72,'S10'!$E$6:$E$13,"Ambos")+COUNTIFS('Holgura'!$B$6:$B$11,$A72,'Holgura'!$E$6:$E$11,"Diego")+COUNTIFS('Holgura'!$B$6:$B$11,$A72,'Holgura'!$E$6:$E$11,"Ambos")+COUNTIFS('Entrega'!$B$6:$B$9,$A72,'Entrega'!$E$6:$E$9,"Diego")+COUNTIFS('Entrega'!$B$6:$B$9,$A72,'Entrega'!$E$6:$E$9,"Ambos")+COUNTIFS('Defensa'!$B$6:$B$10,$A72,'Defensa'!$E$6:$E$10,"Diego")+COUNTIFS('Defensa'!$B$6:$B$10,$A72,'Defensa'!$E$6:$E$10,"Ambos")</f>
         <v/>
       </c>
     </row>
@@ -10652,19 +10673,19 @@
         <v/>
       </c>
       <c r="D73" s="21">
-        <f>SUMIFS('S1'!$I$6:$I$32,'S1'!$B$6:$B$32,$A73,'S1'!$E$6:$E$32,"Víctor")+SUMIFS('S1'!$I$6:$I$32,'S1'!$B$6:$B$32,$A73,'S1'!$E$6:$E$32,"Ambos")+SUMIFS('S2'!$I$6:$I$23,'S2'!$B$6:$B$23,$A73,'S2'!$E$6:$E$23,"Víctor")+SUMIFS('S2'!$I$6:$I$23,'S2'!$B$6:$B$23,$A73,'S2'!$E$6:$E$23,"Ambos")+SUMIFS('S3'!$I$6:$I$19,'S3'!$B$6:$B$19,$A73,'S3'!$E$6:$E$19,"Víctor")+SUMIFS('S3'!$I$6:$I$19,'S3'!$B$6:$B$19,$A73,'S3'!$E$6:$E$19,"Ambos")+SUMIFS('S4'!$I$6:$I$20,'S4'!$B$6:$B$20,$A73,'S4'!$E$6:$E$20,"Víctor")+SUMIFS('S4'!$I$6:$I$20,'S4'!$B$6:$B$20,$A73,'S4'!$E$6:$E$20,"Ambos")+SUMIFS('S5'!$I$6:$I$20,'S5'!$B$6:$B$20,$A73,'S5'!$E$6:$E$20,"Víctor")+SUMIFS('S5'!$I$6:$I$20,'S5'!$B$6:$B$20,$A73,'S5'!$E$6:$E$20,"Ambos")+SUMIFS('S6'!$I$6:$I$17,'S6'!$B$6:$B$17,$A73,'S6'!$E$6:$E$17,"Víctor")+SUMIFS('S6'!$I$6:$I$17,'S6'!$B$6:$B$17,$A73,'S6'!$E$6:$E$17,"Ambos")+SUMIFS('S7'!$I$6:$I$19,'S7'!$B$6:$B$19,$A73,'S7'!$E$6:$E$19,"Víctor")+SUMIFS('S7'!$I$6:$I$19,'S7'!$B$6:$B$19,$A73,'S7'!$E$6:$E$19,"Ambos")+SUMIFS('S8'!$I$6:$I$23,'S8'!$B$6:$B$23,$A73,'S8'!$E$6:$E$23,"Víctor")+SUMIFS('S8'!$I$6:$I$23,'S8'!$B$6:$B$23,$A73,'S8'!$E$6:$E$23,"Ambos")+SUMIFS('S9'!$I$6:$I$15,'S9'!$B$6:$B$15,$A73,'S9'!$E$6:$E$15,"Víctor")+SUMIFS('S9'!$I$6:$I$15,'S9'!$B$6:$B$15,$A73,'S9'!$E$6:$E$15,"Ambos")+SUMIFS('S10'!$I$6:$I$13,'S10'!$B$6:$B$13,$A73,'S10'!$E$6:$E$13,"Víctor")+SUMIFS('S10'!$I$6:$I$13,'S10'!$B$6:$B$13,$A73,'S10'!$E$6:$E$13,"Ambos")+SUMIFS('Holgura'!$I$6:$I$11,'Holgura'!$B$6:$B$11,$A73,'Holgura'!$E$6:$E$11,"Víctor")+SUMIFS('Holgura'!$I$6:$I$11,'Holgura'!$B$6:$B$11,$A73,'Holgura'!$E$6:$E$11,"Ambos")+SUMIFS('Entrega'!$I$6:$I$9,'Entrega'!$B$6:$B$9,$A73,'Entrega'!$E$6:$E$9,"Víctor")+SUMIFS('Entrega'!$I$6:$I$9,'Entrega'!$B$6:$B$9,$A73,'Entrega'!$E$6:$E$9,"Ambos")+SUMIFS('Defensa'!$I$6:$I$10,'Defensa'!$B$6:$B$10,$A73,'Defensa'!$E$6:$E$10,"Víctor")+SUMIFS('Defensa'!$I$6:$I$10,'Defensa'!$B$6:$B$10,$A73,'Defensa'!$E$6:$E$10,"Ambos")</f>
+        <f>SUMIFS('S1'!$I$6:$I$32,'S1'!$B$6:$B$32,$A73,'S1'!$E$6:$E$32,"Víctor")+SUMIFS('S1'!$I$6:$I$32,'S1'!$B$6:$B$32,$A73,'S1'!$E$6:$E$32,"Ambos")+SUMIFS('S2'!$I$6:$I$23,'S2'!$B$6:$B$23,$A73,'S2'!$E$6:$E$23,"Víctor")+SUMIFS('S2'!$I$6:$I$23,'S2'!$B$6:$B$23,$A73,'S2'!$E$6:$E$23,"Ambos")+SUMIFS('S3'!$I$6:$I$24,'S3'!$B$6:$B$24,$A73,'S3'!$E$6:$E$24,"Víctor")+SUMIFS('S3'!$I$6:$I$24,'S3'!$B$6:$B$24,$A73,'S3'!$E$6:$E$24,"Ambos")+SUMIFS('S4'!$I$6:$I$22,'S4'!$B$6:$B$22,$A73,'S4'!$E$6:$E$22,"Víctor")+SUMIFS('S4'!$I$6:$I$22,'S4'!$B$6:$B$22,$A73,'S4'!$E$6:$E$22,"Ambos")+SUMIFS('S5'!$I$6:$I$20,'S5'!$B$6:$B$20,$A73,'S5'!$E$6:$E$20,"Víctor")+SUMIFS('S5'!$I$6:$I$20,'S5'!$B$6:$B$20,$A73,'S5'!$E$6:$E$20,"Ambos")+SUMIFS('S6'!$I$6:$I$17,'S6'!$B$6:$B$17,$A73,'S6'!$E$6:$E$17,"Víctor")+SUMIFS('S6'!$I$6:$I$17,'S6'!$B$6:$B$17,$A73,'S6'!$E$6:$E$17,"Ambos")+SUMIFS('S7'!$I$6:$I$19,'S7'!$B$6:$B$19,$A73,'S7'!$E$6:$E$19,"Víctor")+SUMIFS('S7'!$I$6:$I$19,'S7'!$B$6:$B$19,$A73,'S7'!$E$6:$E$19,"Ambos")+SUMIFS('S8'!$I$6:$I$23,'S8'!$B$6:$B$23,$A73,'S8'!$E$6:$E$23,"Víctor")+SUMIFS('S8'!$I$6:$I$23,'S8'!$B$6:$B$23,$A73,'S8'!$E$6:$E$23,"Ambos")+SUMIFS('S9'!$I$6:$I$15,'S9'!$B$6:$B$15,$A73,'S9'!$E$6:$E$15,"Víctor")+SUMIFS('S9'!$I$6:$I$15,'S9'!$B$6:$B$15,$A73,'S9'!$E$6:$E$15,"Ambos")+SUMIFS('S10'!$I$6:$I$13,'S10'!$B$6:$B$13,$A73,'S10'!$E$6:$E$13,"Víctor")+SUMIFS('S10'!$I$6:$I$13,'S10'!$B$6:$B$13,$A73,'S10'!$E$6:$E$13,"Ambos")+SUMIFS('Holgura'!$I$6:$I$11,'Holgura'!$B$6:$B$11,$A73,'Holgura'!$E$6:$E$11,"Víctor")+SUMIFS('Holgura'!$I$6:$I$11,'Holgura'!$B$6:$B$11,$A73,'Holgura'!$E$6:$E$11,"Ambos")+SUMIFS('Entrega'!$I$6:$I$9,'Entrega'!$B$6:$B$9,$A73,'Entrega'!$E$6:$E$9,"Víctor")+SUMIFS('Entrega'!$I$6:$I$9,'Entrega'!$B$6:$B$9,$A73,'Entrega'!$E$6:$E$9,"Ambos")+SUMIFS('Defensa'!$I$6:$I$10,'Defensa'!$B$6:$B$10,$A73,'Defensa'!$E$6:$E$10,"Víctor")+SUMIFS('Defensa'!$I$6:$I$10,'Defensa'!$B$6:$B$10,$A73,'Defensa'!$E$6:$E$10,"Ambos")</f>
         <v/>
       </c>
       <c r="E73" s="21">
-        <f>SUMIFS('S1'!$I$6:$I$32,'S1'!$B$6:$B$32,$A73,'S1'!$E$6:$E$32,"Diego")+SUMIFS('S1'!$I$6:$I$32,'S1'!$B$6:$B$32,$A73,'S1'!$E$6:$E$32,"Ambos")+SUMIFS('S2'!$I$6:$I$23,'S2'!$B$6:$B$23,$A73,'S2'!$E$6:$E$23,"Diego")+SUMIFS('S2'!$I$6:$I$23,'S2'!$B$6:$B$23,$A73,'S2'!$E$6:$E$23,"Ambos")+SUMIFS('S3'!$I$6:$I$19,'S3'!$B$6:$B$19,$A73,'S3'!$E$6:$E$19,"Diego")+SUMIFS('S3'!$I$6:$I$19,'S3'!$B$6:$B$19,$A73,'S3'!$E$6:$E$19,"Ambos")+SUMIFS('S4'!$I$6:$I$20,'S4'!$B$6:$B$20,$A73,'S4'!$E$6:$E$20,"Diego")+SUMIFS('S4'!$I$6:$I$20,'S4'!$B$6:$B$20,$A73,'S4'!$E$6:$E$20,"Ambos")+SUMIFS('S5'!$I$6:$I$20,'S5'!$B$6:$B$20,$A73,'S5'!$E$6:$E$20,"Diego")+SUMIFS('S5'!$I$6:$I$20,'S5'!$B$6:$B$20,$A73,'S5'!$E$6:$E$20,"Ambos")+SUMIFS('S6'!$I$6:$I$17,'S6'!$B$6:$B$17,$A73,'S6'!$E$6:$E$17,"Diego")+SUMIFS('S6'!$I$6:$I$17,'S6'!$B$6:$B$17,$A73,'S6'!$E$6:$E$17,"Ambos")+SUMIFS('S7'!$I$6:$I$19,'S7'!$B$6:$B$19,$A73,'S7'!$E$6:$E$19,"Diego")+SUMIFS('S7'!$I$6:$I$19,'S7'!$B$6:$B$19,$A73,'S7'!$E$6:$E$19,"Ambos")+SUMIFS('S8'!$I$6:$I$23,'S8'!$B$6:$B$23,$A73,'S8'!$E$6:$E$23,"Diego")+SUMIFS('S8'!$I$6:$I$23,'S8'!$B$6:$B$23,$A73,'S8'!$E$6:$E$23,"Ambos")+SUMIFS('S9'!$I$6:$I$15,'S9'!$B$6:$B$15,$A73,'S9'!$E$6:$E$15,"Diego")+SUMIFS('S9'!$I$6:$I$15,'S9'!$B$6:$B$15,$A73,'S9'!$E$6:$E$15,"Ambos")+SUMIFS('S10'!$I$6:$I$13,'S10'!$B$6:$B$13,$A73,'S10'!$E$6:$E$13,"Diego")+SUMIFS('S10'!$I$6:$I$13,'S10'!$B$6:$B$13,$A73,'S10'!$E$6:$E$13,"Ambos")+SUMIFS('Holgura'!$I$6:$I$11,'Holgura'!$B$6:$B$11,$A73,'Holgura'!$E$6:$E$11,"Diego")+SUMIFS('Holgura'!$I$6:$I$11,'Holgura'!$B$6:$B$11,$A73,'Holgura'!$E$6:$E$11,"Ambos")+SUMIFS('Entrega'!$I$6:$I$9,'Entrega'!$B$6:$B$9,$A73,'Entrega'!$E$6:$E$9,"Diego")+SUMIFS('Entrega'!$I$6:$I$9,'Entrega'!$B$6:$B$9,$A73,'Entrega'!$E$6:$E$9,"Ambos")+SUMIFS('Defensa'!$I$6:$I$10,'Defensa'!$B$6:$B$10,$A73,'Defensa'!$E$6:$E$10,"Diego")+SUMIFS('Defensa'!$I$6:$I$10,'Defensa'!$B$6:$B$10,$A73,'Defensa'!$E$6:$E$10,"Ambos")</f>
+        <f>SUMIFS('S1'!$I$6:$I$32,'S1'!$B$6:$B$32,$A73,'S1'!$E$6:$E$32,"Diego")+SUMIFS('S1'!$I$6:$I$32,'S1'!$B$6:$B$32,$A73,'S1'!$E$6:$E$32,"Ambos")+SUMIFS('S2'!$I$6:$I$23,'S2'!$B$6:$B$23,$A73,'S2'!$E$6:$E$23,"Diego")+SUMIFS('S2'!$I$6:$I$23,'S2'!$B$6:$B$23,$A73,'S2'!$E$6:$E$23,"Ambos")+SUMIFS('S3'!$I$6:$I$24,'S3'!$B$6:$B$24,$A73,'S3'!$E$6:$E$24,"Diego")+SUMIFS('S3'!$I$6:$I$24,'S3'!$B$6:$B$24,$A73,'S3'!$E$6:$E$24,"Ambos")+SUMIFS('S4'!$I$6:$I$22,'S4'!$B$6:$B$22,$A73,'S4'!$E$6:$E$22,"Diego")+SUMIFS('S4'!$I$6:$I$22,'S4'!$B$6:$B$22,$A73,'S4'!$E$6:$E$22,"Ambos")+SUMIFS('S5'!$I$6:$I$20,'S5'!$B$6:$B$20,$A73,'S5'!$E$6:$E$20,"Diego")+SUMIFS('S5'!$I$6:$I$20,'S5'!$B$6:$B$20,$A73,'S5'!$E$6:$E$20,"Ambos")+SUMIFS('S6'!$I$6:$I$17,'S6'!$B$6:$B$17,$A73,'S6'!$E$6:$E$17,"Diego")+SUMIFS('S6'!$I$6:$I$17,'S6'!$B$6:$B$17,$A73,'S6'!$E$6:$E$17,"Ambos")+SUMIFS('S7'!$I$6:$I$19,'S7'!$B$6:$B$19,$A73,'S7'!$E$6:$E$19,"Diego")+SUMIFS('S7'!$I$6:$I$19,'S7'!$B$6:$B$19,$A73,'S7'!$E$6:$E$19,"Ambos")+SUMIFS('S8'!$I$6:$I$23,'S8'!$B$6:$B$23,$A73,'S8'!$E$6:$E$23,"Diego")+SUMIFS('S8'!$I$6:$I$23,'S8'!$B$6:$B$23,$A73,'S8'!$E$6:$E$23,"Ambos")+SUMIFS('S9'!$I$6:$I$15,'S9'!$B$6:$B$15,$A73,'S9'!$E$6:$E$15,"Diego")+SUMIFS('S9'!$I$6:$I$15,'S9'!$B$6:$B$15,$A73,'S9'!$E$6:$E$15,"Ambos")+SUMIFS('S10'!$I$6:$I$13,'S10'!$B$6:$B$13,$A73,'S10'!$E$6:$E$13,"Diego")+SUMIFS('S10'!$I$6:$I$13,'S10'!$B$6:$B$13,$A73,'S10'!$E$6:$E$13,"Ambos")+SUMIFS('Holgura'!$I$6:$I$11,'Holgura'!$B$6:$B$11,$A73,'Holgura'!$E$6:$E$11,"Diego")+SUMIFS('Holgura'!$I$6:$I$11,'Holgura'!$B$6:$B$11,$A73,'Holgura'!$E$6:$E$11,"Ambos")+SUMIFS('Entrega'!$I$6:$I$9,'Entrega'!$B$6:$B$9,$A73,'Entrega'!$E$6:$E$9,"Diego")+SUMIFS('Entrega'!$I$6:$I$9,'Entrega'!$B$6:$B$9,$A73,'Entrega'!$E$6:$E$9,"Ambos")+SUMIFS('Defensa'!$I$6:$I$10,'Defensa'!$B$6:$B$10,$A73,'Defensa'!$E$6:$E$10,"Diego")+SUMIFS('Defensa'!$I$6:$I$10,'Defensa'!$B$6:$B$10,$A73,'Defensa'!$E$6:$E$10,"Ambos")</f>
         <v/>
       </c>
       <c r="F73" s="21">
-        <f>COUNTIFS('S1'!$B$6:$B$32,$A73,'S1'!$E$6:$E$32,"Víctor")+COUNTIFS('S1'!$B$6:$B$32,$A73,'S1'!$E$6:$E$32,"Ambos")+COUNTIFS('S2'!$B$6:$B$23,$A73,'S2'!$E$6:$E$23,"Víctor")+COUNTIFS('S2'!$B$6:$B$23,$A73,'S2'!$E$6:$E$23,"Ambos")+COUNTIFS('S3'!$B$6:$B$19,$A73,'S3'!$E$6:$E$19,"Víctor")+COUNTIFS('S3'!$B$6:$B$19,$A73,'S3'!$E$6:$E$19,"Ambos")+COUNTIFS('S4'!$B$6:$B$20,$A73,'S4'!$E$6:$E$20,"Víctor")+COUNTIFS('S4'!$B$6:$B$20,$A73,'S4'!$E$6:$E$20,"Ambos")+COUNTIFS('S5'!$B$6:$B$20,$A73,'S5'!$E$6:$E$20,"Víctor")+COUNTIFS('S5'!$B$6:$B$20,$A73,'S5'!$E$6:$E$20,"Ambos")+COUNTIFS('S6'!$B$6:$B$17,$A73,'S6'!$E$6:$E$17,"Víctor")+COUNTIFS('S6'!$B$6:$B$17,$A73,'S6'!$E$6:$E$17,"Ambos")+COUNTIFS('S7'!$B$6:$B$19,$A73,'S7'!$E$6:$E$19,"Víctor")+COUNTIFS('S7'!$B$6:$B$19,$A73,'S7'!$E$6:$E$19,"Ambos")+COUNTIFS('S8'!$B$6:$B$23,$A73,'S8'!$E$6:$E$23,"Víctor")+COUNTIFS('S8'!$B$6:$B$23,$A73,'S8'!$E$6:$E$23,"Ambos")+COUNTIFS('S9'!$B$6:$B$15,$A73,'S9'!$E$6:$E$15,"Víctor")+COUNTIFS('S9'!$B$6:$B$15,$A73,'S9'!$E$6:$E$15,"Ambos")+COUNTIFS('S10'!$B$6:$B$13,$A73,'S10'!$E$6:$E$13,"Víctor")+COUNTIFS('S10'!$B$6:$B$13,$A73,'S10'!$E$6:$E$13,"Ambos")+COUNTIFS('Holgura'!$B$6:$B$11,$A73,'Holgura'!$E$6:$E$11,"Víctor")+COUNTIFS('Holgura'!$B$6:$B$11,$A73,'Holgura'!$E$6:$E$11,"Ambos")+COUNTIFS('Entrega'!$B$6:$B$9,$A73,'Entrega'!$E$6:$E$9,"Víctor")+COUNTIFS('Entrega'!$B$6:$B$9,$A73,'Entrega'!$E$6:$E$9,"Ambos")+COUNTIFS('Defensa'!$B$6:$B$10,$A73,'Defensa'!$E$6:$E$10,"Víctor")+COUNTIFS('Defensa'!$B$6:$B$10,$A73,'Defensa'!$E$6:$E$10,"Ambos")</f>
+        <f>COUNTIFS('S1'!$B$6:$B$32,$A73,'S1'!$E$6:$E$32,"Víctor")+COUNTIFS('S1'!$B$6:$B$32,$A73,'S1'!$E$6:$E$32,"Ambos")+COUNTIFS('S2'!$B$6:$B$23,$A73,'S2'!$E$6:$E$23,"Víctor")+COUNTIFS('S2'!$B$6:$B$23,$A73,'S2'!$E$6:$E$23,"Ambos")+COUNTIFS('S3'!$B$6:$B$24,$A73,'S3'!$E$6:$E$24,"Víctor")+COUNTIFS('S3'!$B$6:$B$24,$A73,'S3'!$E$6:$E$24,"Ambos")+COUNTIFS('S4'!$B$6:$B$22,$A73,'S4'!$E$6:$E$22,"Víctor")+COUNTIFS('S4'!$B$6:$B$22,$A73,'S4'!$E$6:$E$22,"Ambos")+COUNTIFS('S5'!$B$6:$B$20,$A73,'S5'!$E$6:$E$20,"Víctor")+COUNTIFS('S5'!$B$6:$B$20,$A73,'S5'!$E$6:$E$20,"Ambos")+COUNTIFS('S6'!$B$6:$B$17,$A73,'S6'!$E$6:$E$17,"Víctor")+COUNTIFS('S6'!$B$6:$B$17,$A73,'S6'!$E$6:$E$17,"Ambos")+COUNTIFS('S7'!$B$6:$B$19,$A73,'S7'!$E$6:$E$19,"Víctor")+COUNTIFS('S7'!$B$6:$B$19,$A73,'S7'!$E$6:$E$19,"Ambos")+COUNTIFS('S8'!$B$6:$B$23,$A73,'S8'!$E$6:$E$23,"Víctor")+COUNTIFS('S8'!$B$6:$B$23,$A73,'S8'!$E$6:$E$23,"Ambos")+COUNTIFS('S9'!$B$6:$B$15,$A73,'S9'!$E$6:$E$15,"Víctor")+COUNTIFS('S9'!$B$6:$B$15,$A73,'S9'!$E$6:$E$15,"Ambos")+COUNTIFS('S10'!$B$6:$B$13,$A73,'S10'!$E$6:$E$13,"Víctor")+COUNTIFS('S10'!$B$6:$B$13,$A73,'S10'!$E$6:$E$13,"Ambos")+COUNTIFS('Holgura'!$B$6:$B$11,$A73,'Holgura'!$E$6:$E$11,"Víctor")+COUNTIFS('Holgura'!$B$6:$B$11,$A73,'Holgura'!$E$6:$E$11,"Ambos")+COUNTIFS('Entrega'!$B$6:$B$9,$A73,'Entrega'!$E$6:$E$9,"Víctor")+COUNTIFS('Entrega'!$B$6:$B$9,$A73,'Entrega'!$E$6:$E$9,"Ambos")+COUNTIFS('Defensa'!$B$6:$B$10,$A73,'Defensa'!$E$6:$E$10,"Víctor")+COUNTIFS('Defensa'!$B$6:$B$10,$A73,'Defensa'!$E$6:$E$10,"Ambos")</f>
         <v/>
       </c>
       <c r="G73" s="21">
-        <f>COUNTIFS('S1'!$B$6:$B$32,$A73,'S1'!$E$6:$E$32,"Diego")+COUNTIFS('S1'!$B$6:$B$32,$A73,'S1'!$E$6:$E$32,"Ambos")+COUNTIFS('S2'!$B$6:$B$23,$A73,'S2'!$E$6:$E$23,"Diego")+COUNTIFS('S2'!$B$6:$B$23,$A73,'S2'!$E$6:$E$23,"Ambos")+COUNTIFS('S3'!$B$6:$B$19,$A73,'S3'!$E$6:$E$19,"Diego")+COUNTIFS('S3'!$B$6:$B$19,$A73,'S3'!$E$6:$E$19,"Ambos")+COUNTIFS('S4'!$B$6:$B$20,$A73,'S4'!$E$6:$E$20,"Diego")+COUNTIFS('S4'!$B$6:$B$20,$A73,'S4'!$E$6:$E$20,"Ambos")+COUNTIFS('S5'!$B$6:$B$20,$A73,'S5'!$E$6:$E$20,"Diego")+COUNTIFS('S5'!$B$6:$B$20,$A73,'S5'!$E$6:$E$20,"Ambos")+COUNTIFS('S6'!$B$6:$B$17,$A73,'S6'!$E$6:$E$17,"Diego")+COUNTIFS('S6'!$B$6:$B$17,$A73,'S6'!$E$6:$E$17,"Ambos")+COUNTIFS('S7'!$B$6:$B$19,$A73,'S7'!$E$6:$E$19,"Diego")+COUNTIFS('S7'!$B$6:$B$19,$A73,'S7'!$E$6:$E$19,"Ambos")+COUNTIFS('S8'!$B$6:$B$23,$A73,'S8'!$E$6:$E$23,"Diego")+COUNTIFS('S8'!$B$6:$B$23,$A73,'S8'!$E$6:$E$23,"Ambos")+COUNTIFS('S9'!$B$6:$B$15,$A73,'S9'!$E$6:$E$15,"Diego")+COUNTIFS('S9'!$B$6:$B$15,$A73,'S9'!$E$6:$E$15,"Ambos")+COUNTIFS('S10'!$B$6:$B$13,$A73,'S10'!$E$6:$E$13,"Diego")+COUNTIFS('S10'!$B$6:$B$13,$A73,'S10'!$E$6:$E$13,"Ambos")+COUNTIFS('Holgura'!$B$6:$B$11,$A73,'Holgura'!$E$6:$E$11,"Diego")+COUNTIFS('Holgura'!$B$6:$B$11,$A73,'Holgura'!$E$6:$E$11,"Ambos")+COUNTIFS('Entrega'!$B$6:$B$9,$A73,'Entrega'!$E$6:$E$9,"Diego")+COUNTIFS('Entrega'!$B$6:$B$9,$A73,'Entrega'!$E$6:$E$9,"Ambos")+COUNTIFS('Defensa'!$B$6:$B$10,$A73,'Defensa'!$E$6:$E$10,"Diego")+COUNTIFS('Defensa'!$B$6:$B$10,$A73,'Defensa'!$E$6:$E$10,"Ambos")</f>
+        <f>COUNTIFS('S1'!$B$6:$B$32,$A73,'S1'!$E$6:$E$32,"Diego")+COUNTIFS('S1'!$B$6:$B$32,$A73,'S1'!$E$6:$E$32,"Ambos")+COUNTIFS('S2'!$B$6:$B$23,$A73,'S2'!$E$6:$E$23,"Diego")+COUNTIFS('S2'!$B$6:$B$23,$A73,'S2'!$E$6:$E$23,"Ambos")+COUNTIFS('S3'!$B$6:$B$24,$A73,'S3'!$E$6:$E$24,"Diego")+COUNTIFS('S3'!$B$6:$B$24,$A73,'S3'!$E$6:$E$24,"Ambos")+COUNTIFS('S4'!$B$6:$B$22,$A73,'S4'!$E$6:$E$22,"Diego")+COUNTIFS('S4'!$B$6:$B$22,$A73,'S4'!$E$6:$E$22,"Ambos")+COUNTIFS('S5'!$B$6:$B$20,$A73,'S5'!$E$6:$E$20,"Diego")+COUNTIFS('S5'!$B$6:$B$20,$A73,'S5'!$E$6:$E$20,"Ambos")+COUNTIFS('S6'!$B$6:$B$17,$A73,'S6'!$E$6:$E$17,"Diego")+COUNTIFS('S6'!$B$6:$B$17,$A73,'S6'!$E$6:$E$17,"Ambos")+COUNTIFS('S7'!$B$6:$B$19,$A73,'S7'!$E$6:$E$19,"Diego")+COUNTIFS('S7'!$B$6:$B$19,$A73,'S7'!$E$6:$E$19,"Ambos")+COUNTIFS('S8'!$B$6:$B$23,$A73,'S8'!$E$6:$E$23,"Diego")+COUNTIFS('S8'!$B$6:$B$23,$A73,'S8'!$E$6:$E$23,"Ambos")+COUNTIFS('S9'!$B$6:$B$15,$A73,'S9'!$E$6:$E$15,"Diego")+COUNTIFS('S9'!$B$6:$B$15,$A73,'S9'!$E$6:$E$15,"Ambos")+COUNTIFS('S10'!$B$6:$B$13,$A73,'S10'!$E$6:$E$13,"Diego")+COUNTIFS('S10'!$B$6:$B$13,$A73,'S10'!$E$6:$E$13,"Ambos")+COUNTIFS('Holgura'!$B$6:$B$11,$A73,'Holgura'!$E$6:$E$11,"Diego")+COUNTIFS('Holgura'!$B$6:$B$11,$A73,'Holgura'!$E$6:$E$11,"Ambos")+COUNTIFS('Entrega'!$B$6:$B$9,$A73,'Entrega'!$E$6:$E$9,"Diego")+COUNTIFS('Entrega'!$B$6:$B$9,$A73,'Entrega'!$E$6:$E$9,"Ambos")+COUNTIFS('Defensa'!$B$6:$B$10,$A73,'Defensa'!$E$6:$E$10,"Diego")+COUNTIFS('Defensa'!$B$6:$B$10,$A73,'Defensa'!$E$6:$E$10,"Ambos")</f>
         <v/>
       </c>
     </row>
@@ -10681,19 +10702,19 @@
         <v/>
       </c>
       <c r="D74" s="21">
-        <f>SUMIFS('S1'!$I$6:$I$32,'S1'!$B$6:$B$32,$A74,'S1'!$E$6:$E$32,"Víctor")+SUMIFS('S1'!$I$6:$I$32,'S1'!$B$6:$B$32,$A74,'S1'!$E$6:$E$32,"Ambos")+SUMIFS('S2'!$I$6:$I$23,'S2'!$B$6:$B$23,$A74,'S2'!$E$6:$E$23,"Víctor")+SUMIFS('S2'!$I$6:$I$23,'S2'!$B$6:$B$23,$A74,'S2'!$E$6:$E$23,"Ambos")+SUMIFS('S3'!$I$6:$I$19,'S3'!$B$6:$B$19,$A74,'S3'!$E$6:$E$19,"Víctor")+SUMIFS('S3'!$I$6:$I$19,'S3'!$B$6:$B$19,$A74,'S3'!$E$6:$E$19,"Ambos")+SUMIFS('S4'!$I$6:$I$20,'S4'!$B$6:$B$20,$A74,'S4'!$E$6:$E$20,"Víctor")+SUMIFS('S4'!$I$6:$I$20,'S4'!$B$6:$B$20,$A74,'S4'!$E$6:$E$20,"Ambos")+SUMIFS('S5'!$I$6:$I$20,'S5'!$B$6:$B$20,$A74,'S5'!$E$6:$E$20,"Víctor")+SUMIFS('S5'!$I$6:$I$20,'S5'!$B$6:$B$20,$A74,'S5'!$E$6:$E$20,"Ambos")+SUMIFS('S6'!$I$6:$I$17,'S6'!$B$6:$B$17,$A74,'S6'!$E$6:$E$17,"Víctor")+SUMIFS('S6'!$I$6:$I$17,'S6'!$B$6:$B$17,$A74,'S6'!$E$6:$E$17,"Ambos")+SUMIFS('S7'!$I$6:$I$19,'S7'!$B$6:$B$19,$A74,'S7'!$E$6:$E$19,"Víctor")+SUMIFS('S7'!$I$6:$I$19,'S7'!$B$6:$B$19,$A74,'S7'!$E$6:$E$19,"Ambos")+SUMIFS('S8'!$I$6:$I$23,'S8'!$B$6:$B$23,$A74,'S8'!$E$6:$E$23,"Víctor")+SUMIFS('S8'!$I$6:$I$23,'S8'!$B$6:$B$23,$A74,'S8'!$E$6:$E$23,"Ambos")+SUMIFS('S9'!$I$6:$I$15,'S9'!$B$6:$B$15,$A74,'S9'!$E$6:$E$15,"Víctor")+SUMIFS('S9'!$I$6:$I$15,'S9'!$B$6:$B$15,$A74,'S9'!$E$6:$E$15,"Ambos")+SUMIFS('S10'!$I$6:$I$13,'S10'!$B$6:$B$13,$A74,'S10'!$E$6:$E$13,"Víctor")+SUMIFS('S10'!$I$6:$I$13,'S10'!$B$6:$B$13,$A74,'S10'!$E$6:$E$13,"Ambos")+SUMIFS('Holgura'!$I$6:$I$11,'Holgura'!$B$6:$B$11,$A74,'Holgura'!$E$6:$E$11,"Víctor")+SUMIFS('Holgura'!$I$6:$I$11,'Holgura'!$B$6:$B$11,$A74,'Holgura'!$E$6:$E$11,"Ambos")+SUMIFS('Entrega'!$I$6:$I$9,'Entrega'!$B$6:$B$9,$A74,'Entrega'!$E$6:$E$9,"Víctor")+SUMIFS('Entrega'!$I$6:$I$9,'Entrega'!$B$6:$B$9,$A74,'Entrega'!$E$6:$E$9,"Ambos")+SUMIFS('Defensa'!$I$6:$I$10,'Defensa'!$B$6:$B$10,$A74,'Defensa'!$E$6:$E$10,"Víctor")+SUMIFS('Defensa'!$I$6:$I$10,'Defensa'!$B$6:$B$10,$A74,'Defensa'!$E$6:$E$10,"Ambos")</f>
+        <f>SUMIFS('S1'!$I$6:$I$32,'S1'!$B$6:$B$32,$A74,'S1'!$E$6:$E$32,"Víctor")+SUMIFS('S1'!$I$6:$I$32,'S1'!$B$6:$B$32,$A74,'S1'!$E$6:$E$32,"Ambos")+SUMIFS('S2'!$I$6:$I$23,'S2'!$B$6:$B$23,$A74,'S2'!$E$6:$E$23,"Víctor")+SUMIFS('S2'!$I$6:$I$23,'S2'!$B$6:$B$23,$A74,'S2'!$E$6:$E$23,"Ambos")+SUMIFS('S3'!$I$6:$I$24,'S3'!$B$6:$B$24,$A74,'S3'!$E$6:$E$24,"Víctor")+SUMIFS('S3'!$I$6:$I$24,'S3'!$B$6:$B$24,$A74,'S3'!$E$6:$E$24,"Ambos")+SUMIFS('S4'!$I$6:$I$22,'S4'!$B$6:$B$22,$A74,'S4'!$E$6:$E$22,"Víctor")+SUMIFS('S4'!$I$6:$I$22,'S4'!$B$6:$B$22,$A74,'S4'!$E$6:$E$22,"Ambos")+SUMIFS('S5'!$I$6:$I$20,'S5'!$B$6:$B$20,$A74,'S5'!$E$6:$E$20,"Víctor")+SUMIFS('S5'!$I$6:$I$20,'S5'!$B$6:$B$20,$A74,'S5'!$E$6:$E$20,"Ambos")+SUMIFS('S6'!$I$6:$I$17,'S6'!$B$6:$B$17,$A74,'S6'!$E$6:$E$17,"Víctor")+SUMIFS('S6'!$I$6:$I$17,'S6'!$B$6:$B$17,$A74,'S6'!$E$6:$E$17,"Ambos")+SUMIFS('S7'!$I$6:$I$19,'S7'!$B$6:$B$19,$A74,'S7'!$E$6:$E$19,"Víctor")+SUMIFS('S7'!$I$6:$I$19,'S7'!$B$6:$B$19,$A74,'S7'!$E$6:$E$19,"Ambos")+SUMIFS('S8'!$I$6:$I$23,'S8'!$B$6:$B$23,$A74,'S8'!$E$6:$E$23,"Víctor")+SUMIFS('S8'!$I$6:$I$23,'S8'!$B$6:$B$23,$A74,'S8'!$E$6:$E$23,"Ambos")+SUMIFS('S9'!$I$6:$I$15,'S9'!$B$6:$B$15,$A74,'S9'!$E$6:$E$15,"Víctor")+SUMIFS('S9'!$I$6:$I$15,'S9'!$B$6:$B$15,$A74,'S9'!$E$6:$E$15,"Ambos")+SUMIFS('S10'!$I$6:$I$13,'S10'!$B$6:$B$13,$A74,'S10'!$E$6:$E$13,"Víctor")+SUMIFS('S10'!$I$6:$I$13,'S10'!$B$6:$B$13,$A74,'S10'!$E$6:$E$13,"Ambos")+SUMIFS('Holgura'!$I$6:$I$11,'Holgura'!$B$6:$B$11,$A74,'Holgura'!$E$6:$E$11,"Víctor")+SUMIFS('Holgura'!$I$6:$I$11,'Holgura'!$B$6:$B$11,$A74,'Holgura'!$E$6:$E$11,"Ambos")+SUMIFS('Entrega'!$I$6:$I$9,'Entrega'!$B$6:$B$9,$A74,'Entrega'!$E$6:$E$9,"Víctor")+SUMIFS('Entrega'!$I$6:$I$9,'Entrega'!$B$6:$B$9,$A74,'Entrega'!$E$6:$E$9,"Ambos")+SUMIFS('Defensa'!$I$6:$I$10,'Defensa'!$B$6:$B$10,$A74,'Defensa'!$E$6:$E$10,"Víctor")+SUMIFS('Defensa'!$I$6:$I$10,'Defensa'!$B$6:$B$10,$A74,'Defensa'!$E$6:$E$10,"Ambos")</f>
         <v/>
       </c>
       <c r="E74" s="21">
-        <f>SUMIFS('S1'!$I$6:$I$32,'S1'!$B$6:$B$32,$A74,'S1'!$E$6:$E$32,"Diego")+SUMIFS('S1'!$I$6:$I$32,'S1'!$B$6:$B$32,$A74,'S1'!$E$6:$E$32,"Ambos")+SUMIFS('S2'!$I$6:$I$23,'S2'!$B$6:$B$23,$A74,'S2'!$E$6:$E$23,"Diego")+SUMIFS('S2'!$I$6:$I$23,'S2'!$B$6:$B$23,$A74,'S2'!$E$6:$E$23,"Ambos")+SUMIFS('S3'!$I$6:$I$19,'S3'!$B$6:$B$19,$A74,'S3'!$E$6:$E$19,"Diego")+SUMIFS('S3'!$I$6:$I$19,'S3'!$B$6:$B$19,$A74,'S3'!$E$6:$E$19,"Ambos")+SUMIFS('S4'!$I$6:$I$20,'S4'!$B$6:$B$20,$A74,'S4'!$E$6:$E$20,"Diego")+SUMIFS('S4'!$I$6:$I$20,'S4'!$B$6:$B$20,$A74,'S4'!$E$6:$E$20,"Ambos")+SUMIFS('S5'!$I$6:$I$20,'S5'!$B$6:$B$20,$A74,'S5'!$E$6:$E$20,"Diego")+SUMIFS('S5'!$I$6:$I$20,'S5'!$B$6:$B$20,$A74,'S5'!$E$6:$E$20,"Ambos")+SUMIFS('S6'!$I$6:$I$17,'S6'!$B$6:$B$17,$A74,'S6'!$E$6:$E$17,"Diego")+SUMIFS('S6'!$I$6:$I$17,'S6'!$B$6:$B$17,$A74,'S6'!$E$6:$E$17,"Ambos")+SUMIFS('S7'!$I$6:$I$19,'S7'!$B$6:$B$19,$A74,'S7'!$E$6:$E$19,"Diego")+SUMIFS('S7'!$I$6:$I$19,'S7'!$B$6:$B$19,$A74,'S7'!$E$6:$E$19,"Ambos")+SUMIFS('S8'!$I$6:$I$23,'S8'!$B$6:$B$23,$A74,'S8'!$E$6:$E$23,"Diego")+SUMIFS('S8'!$I$6:$I$23,'S8'!$B$6:$B$23,$A74,'S8'!$E$6:$E$23,"Ambos")+SUMIFS('S9'!$I$6:$I$15,'S9'!$B$6:$B$15,$A74,'S9'!$E$6:$E$15,"Diego")+SUMIFS('S9'!$I$6:$I$15,'S9'!$B$6:$B$15,$A74,'S9'!$E$6:$E$15,"Ambos")+SUMIFS('S10'!$I$6:$I$13,'S10'!$B$6:$B$13,$A74,'S10'!$E$6:$E$13,"Diego")+SUMIFS('S10'!$I$6:$I$13,'S10'!$B$6:$B$13,$A74,'S10'!$E$6:$E$13,"Ambos")+SUMIFS('Holgura'!$I$6:$I$11,'Holgura'!$B$6:$B$11,$A74,'Holgura'!$E$6:$E$11,"Diego")+SUMIFS('Holgura'!$I$6:$I$11,'Holgura'!$B$6:$B$11,$A74,'Holgura'!$E$6:$E$11,"Ambos")+SUMIFS('Entrega'!$I$6:$I$9,'Entrega'!$B$6:$B$9,$A74,'Entrega'!$E$6:$E$9,"Diego")+SUMIFS('Entrega'!$I$6:$I$9,'Entrega'!$B$6:$B$9,$A74,'Entrega'!$E$6:$E$9,"Ambos")+SUMIFS('Defensa'!$I$6:$I$10,'Defensa'!$B$6:$B$10,$A74,'Defensa'!$E$6:$E$10,"Diego")+SUMIFS('Defensa'!$I$6:$I$10,'Defensa'!$B$6:$B$10,$A74,'Defensa'!$E$6:$E$10,"Ambos")</f>
+        <f>SUMIFS('S1'!$I$6:$I$32,'S1'!$B$6:$B$32,$A74,'S1'!$E$6:$E$32,"Diego")+SUMIFS('S1'!$I$6:$I$32,'S1'!$B$6:$B$32,$A74,'S1'!$E$6:$E$32,"Ambos")+SUMIFS('S2'!$I$6:$I$23,'S2'!$B$6:$B$23,$A74,'S2'!$E$6:$E$23,"Diego")+SUMIFS('S2'!$I$6:$I$23,'S2'!$B$6:$B$23,$A74,'S2'!$E$6:$E$23,"Ambos")+SUMIFS('S3'!$I$6:$I$24,'S3'!$B$6:$B$24,$A74,'S3'!$E$6:$E$24,"Diego")+SUMIFS('S3'!$I$6:$I$24,'S3'!$B$6:$B$24,$A74,'S3'!$E$6:$E$24,"Ambos")+SUMIFS('S4'!$I$6:$I$22,'S4'!$B$6:$B$22,$A74,'S4'!$E$6:$E$22,"Diego")+SUMIFS('S4'!$I$6:$I$22,'S4'!$B$6:$B$22,$A74,'S4'!$E$6:$E$22,"Ambos")+SUMIFS('S5'!$I$6:$I$20,'S5'!$B$6:$B$20,$A74,'S5'!$E$6:$E$20,"Diego")+SUMIFS('S5'!$I$6:$I$20,'S5'!$B$6:$B$20,$A74,'S5'!$E$6:$E$20,"Ambos")+SUMIFS('S6'!$I$6:$I$17,'S6'!$B$6:$B$17,$A74,'S6'!$E$6:$E$17,"Diego")+SUMIFS('S6'!$I$6:$I$17,'S6'!$B$6:$B$17,$A74,'S6'!$E$6:$E$17,"Ambos")+SUMIFS('S7'!$I$6:$I$19,'S7'!$B$6:$B$19,$A74,'S7'!$E$6:$E$19,"Diego")+SUMIFS('S7'!$I$6:$I$19,'S7'!$B$6:$B$19,$A74,'S7'!$E$6:$E$19,"Ambos")+SUMIFS('S8'!$I$6:$I$23,'S8'!$B$6:$B$23,$A74,'S8'!$E$6:$E$23,"Diego")+SUMIFS('S8'!$I$6:$I$23,'S8'!$B$6:$B$23,$A74,'S8'!$E$6:$E$23,"Ambos")+SUMIFS('S9'!$I$6:$I$15,'S9'!$B$6:$B$15,$A74,'S9'!$E$6:$E$15,"Diego")+SUMIFS('S9'!$I$6:$I$15,'S9'!$B$6:$B$15,$A74,'S9'!$E$6:$E$15,"Ambos")+SUMIFS('S10'!$I$6:$I$13,'S10'!$B$6:$B$13,$A74,'S10'!$E$6:$E$13,"Diego")+SUMIFS('S10'!$I$6:$I$13,'S10'!$B$6:$B$13,$A74,'S10'!$E$6:$E$13,"Ambos")+SUMIFS('Holgura'!$I$6:$I$11,'Holgura'!$B$6:$B$11,$A74,'Holgura'!$E$6:$E$11,"Diego")+SUMIFS('Holgura'!$I$6:$I$11,'Holgura'!$B$6:$B$11,$A74,'Holgura'!$E$6:$E$11,"Ambos")+SUMIFS('Entrega'!$I$6:$I$9,'Entrega'!$B$6:$B$9,$A74,'Entrega'!$E$6:$E$9,"Diego")+SUMIFS('Entrega'!$I$6:$I$9,'Entrega'!$B$6:$B$9,$A74,'Entrega'!$E$6:$E$9,"Ambos")+SUMIFS('Defensa'!$I$6:$I$10,'Defensa'!$B$6:$B$10,$A74,'Defensa'!$E$6:$E$10,"Diego")+SUMIFS('Defensa'!$I$6:$I$10,'Defensa'!$B$6:$B$10,$A74,'Defensa'!$E$6:$E$10,"Ambos")</f>
         <v/>
       </c>
       <c r="F74" s="21">
-        <f>COUNTIFS('S1'!$B$6:$B$32,$A74,'S1'!$E$6:$E$32,"Víctor")+COUNTIFS('S1'!$B$6:$B$32,$A74,'S1'!$E$6:$E$32,"Ambos")+COUNTIFS('S2'!$B$6:$B$23,$A74,'S2'!$E$6:$E$23,"Víctor")+COUNTIFS('S2'!$B$6:$B$23,$A74,'S2'!$E$6:$E$23,"Ambos")+COUNTIFS('S3'!$B$6:$B$19,$A74,'S3'!$E$6:$E$19,"Víctor")+COUNTIFS('S3'!$B$6:$B$19,$A74,'S3'!$E$6:$E$19,"Ambos")+COUNTIFS('S4'!$B$6:$B$20,$A74,'S4'!$E$6:$E$20,"Víctor")+COUNTIFS('S4'!$B$6:$B$20,$A74,'S4'!$E$6:$E$20,"Ambos")+COUNTIFS('S5'!$B$6:$B$20,$A74,'S5'!$E$6:$E$20,"Víctor")+COUNTIFS('S5'!$B$6:$B$20,$A74,'S5'!$E$6:$E$20,"Ambos")+COUNTIFS('S6'!$B$6:$B$17,$A74,'S6'!$E$6:$E$17,"Víctor")+COUNTIFS('S6'!$B$6:$B$17,$A74,'S6'!$E$6:$E$17,"Ambos")+COUNTIFS('S7'!$B$6:$B$19,$A74,'S7'!$E$6:$E$19,"Víctor")+COUNTIFS('S7'!$B$6:$B$19,$A74,'S7'!$E$6:$E$19,"Ambos")+COUNTIFS('S8'!$B$6:$B$23,$A74,'S8'!$E$6:$E$23,"Víctor")+COUNTIFS('S8'!$B$6:$B$23,$A74,'S8'!$E$6:$E$23,"Ambos")+COUNTIFS('S9'!$B$6:$B$15,$A74,'S9'!$E$6:$E$15,"Víctor")+COUNTIFS('S9'!$B$6:$B$15,$A74,'S9'!$E$6:$E$15,"Ambos")+COUNTIFS('S10'!$B$6:$B$13,$A74,'S10'!$E$6:$E$13,"Víctor")+COUNTIFS('S10'!$B$6:$B$13,$A74,'S10'!$E$6:$E$13,"Ambos")+COUNTIFS('Holgura'!$B$6:$B$11,$A74,'Holgura'!$E$6:$E$11,"Víctor")+COUNTIFS('Holgura'!$B$6:$B$11,$A74,'Holgura'!$E$6:$E$11,"Ambos")+COUNTIFS('Entrega'!$B$6:$B$9,$A74,'Entrega'!$E$6:$E$9,"Víctor")+COUNTIFS('Entrega'!$B$6:$B$9,$A74,'Entrega'!$E$6:$E$9,"Ambos")+COUNTIFS('Defensa'!$B$6:$B$10,$A74,'Defensa'!$E$6:$E$10,"Víctor")+COUNTIFS('Defensa'!$B$6:$B$10,$A74,'Defensa'!$E$6:$E$10,"Ambos")</f>
+        <f>COUNTIFS('S1'!$B$6:$B$32,$A74,'S1'!$E$6:$E$32,"Víctor")+COUNTIFS('S1'!$B$6:$B$32,$A74,'S1'!$E$6:$E$32,"Ambos")+COUNTIFS('S2'!$B$6:$B$23,$A74,'S2'!$E$6:$E$23,"Víctor")+COUNTIFS('S2'!$B$6:$B$23,$A74,'S2'!$E$6:$E$23,"Ambos")+COUNTIFS('S3'!$B$6:$B$24,$A74,'S3'!$E$6:$E$24,"Víctor")+COUNTIFS('S3'!$B$6:$B$24,$A74,'S3'!$E$6:$E$24,"Ambos")+COUNTIFS('S4'!$B$6:$B$22,$A74,'S4'!$E$6:$E$22,"Víctor")+COUNTIFS('S4'!$B$6:$B$22,$A74,'S4'!$E$6:$E$22,"Ambos")+COUNTIFS('S5'!$B$6:$B$20,$A74,'S5'!$E$6:$E$20,"Víctor")+COUNTIFS('S5'!$B$6:$B$20,$A74,'S5'!$E$6:$E$20,"Ambos")+COUNTIFS('S6'!$B$6:$B$17,$A74,'S6'!$E$6:$E$17,"Víctor")+COUNTIFS('S6'!$B$6:$B$17,$A74,'S6'!$E$6:$E$17,"Ambos")+COUNTIFS('S7'!$B$6:$B$19,$A74,'S7'!$E$6:$E$19,"Víctor")+COUNTIFS('S7'!$B$6:$B$19,$A74,'S7'!$E$6:$E$19,"Ambos")+COUNTIFS('S8'!$B$6:$B$23,$A74,'S8'!$E$6:$E$23,"Víctor")+COUNTIFS('S8'!$B$6:$B$23,$A74,'S8'!$E$6:$E$23,"Ambos")+COUNTIFS('S9'!$B$6:$B$15,$A74,'S9'!$E$6:$E$15,"Víctor")+COUNTIFS('S9'!$B$6:$B$15,$A74,'S9'!$E$6:$E$15,"Ambos")+COUNTIFS('S10'!$B$6:$B$13,$A74,'S10'!$E$6:$E$13,"Víctor")+COUNTIFS('S10'!$B$6:$B$13,$A74,'S10'!$E$6:$E$13,"Ambos")+COUNTIFS('Holgura'!$B$6:$B$11,$A74,'Holgura'!$E$6:$E$11,"Víctor")+COUNTIFS('Holgura'!$B$6:$B$11,$A74,'Holgura'!$E$6:$E$11,"Ambos")+COUNTIFS('Entrega'!$B$6:$B$9,$A74,'Entrega'!$E$6:$E$9,"Víctor")+COUNTIFS('Entrega'!$B$6:$B$9,$A74,'Entrega'!$E$6:$E$9,"Ambos")+COUNTIFS('Defensa'!$B$6:$B$10,$A74,'Defensa'!$E$6:$E$10,"Víctor")+COUNTIFS('Defensa'!$B$6:$B$10,$A74,'Defensa'!$E$6:$E$10,"Ambos")</f>
         <v/>
       </c>
       <c r="G74" s="21">
-        <f>COUNTIFS('S1'!$B$6:$B$32,$A74,'S1'!$E$6:$E$32,"Diego")+COUNTIFS('S1'!$B$6:$B$32,$A74,'S1'!$E$6:$E$32,"Ambos")+COUNTIFS('S2'!$B$6:$B$23,$A74,'S2'!$E$6:$E$23,"Diego")+COUNTIFS('S2'!$B$6:$B$23,$A74,'S2'!$E$6:$E$23,"Ambos")+COUNTIFS('S3'!$B$6:$B$19,$A74,'S3'!$E$6:$E$19,"Diego")+COUNTIFS('S3'!$B$6:$B$19,$A74,'S3'!$E$6:$E$19,"Ambos")+COUNTIFS('S4'!$B$6:$B$20,$A74,'S4'!$E$6:$E$20,"Diego")+COUNTIFS('S4'!$B$6:$B$20,$A74,'S4'!$E$6:$E$20,"Ambos")+COUNTIFS('S5'!$B$6:$B$20,$A74,'S5'!$E$6:$E$20,"Diego")+COUNTIFS('S5'!$B$6:$B$20,$A74,'S5'!$E$6:$E$20,"Ambos")+COUNTIFS('S6'!$B$6:$B$17,$A74,'S6'!$E$6:$E$17,"Diego")+COUNTIFS('S6'!$B$6:$B$17,$A74,'S6'!$E$6:$E$17,"Ambos")+COUNTIFS('S7'!$B$6:$B$19,$A74,'S7'!$E$6:$E$19,"Diego")+COUNTIFS('S7'!$B$6:$B$19,$A74,'S7'!$E$6:$E$19,"Ambos")+COUNTIFS('S8'!$B$6:$B$23,$A74,'S8'!$E$6:$E$23,"Diego")+COUNTIFS('S8'!$B$6:$B$23,$A74,'S8'!$E$6:$E$23,"Ambos")+COUNTIFS('S9'!$B$6:$B$15,$A74,'S9'!$E$6:$E$15,"Diego")+COUNTIFS('S9'!$B$6:$B$15,$A74,'S9'!$E$6:$E$15,"Ambos")+COUNTIFS('S10'!$B$6:$B$13,$A74,'S10'!$E$6:$E$13,"Diego")+COUNTIFS('S10'!$B$6:$B$13,$A74,'S10'!$E$6:$E$13,"Ambos")+COUNTIFS('Holgura'!$B$6:$B$11,$A74,'Holgura'!$E$6:$E$11,"Diego")+COUNTIFS('Holgura'!$B$6:$B$11,$A74,'Holgura'!$E$6:$E$11,"Ambos")+COUNTIFS('Entrega'!$B$6:$B$9,$A74,'Entrega'!$E$6:$E$9,"Diego")+COUNTIFS('Entrega'!$B$6:$B$9,$A74,'Entrega'!$E$6:$E$9,"Ambos")+COUNTIFS('Defensa'!$B$6:$B$10,$A74,'Defensa'!$E$6:$E$10,"Diego")+COUNTIFS('Defensa'!$B$6:$B$10,$A74,'Defensa'!$E$6:$E$10,"Ambos")</f>
+        <f>COUNTIFS('S1'!$B$6:$B$32,$A74,'S1'!$E$6:$E$32,"Diego")+COUNTIFS('S1'!$B$6:$B$32,$A74,'S1'!$E$6:$E$32,"Ambos")+COUNTIFS('S2'!$B$6:$B$23,$A74,'S2'!$E$6:$E$23,"Diego")+COUNTIFS('S2'!$B$6:$B$23,$A74,'S2'!$E$6:$E$23,"Ambos")+COUNTIFS('S3'!$B$6:$B$24,$A74,'S3'!$E$6:$E$24,"Diego")+COUNTIFS('S3'!$B$6:$B$24,$A74,'S3'!$E$6:$E$24,"Ambos")+COUNTIFS('S4'!$B$6:$B$22,$A74,'S4'!$E$6:$E$22,"Diego")+COUNTIFS('S4'!$B$6:$B$22,$A74,'S4'!$E$6:$E$22,"Ambos")+COUNTIFS('S5'!$B$6:$B$20,$A74,'S5'!$E$6:$E$20,"Diego")+COUNTIFS('S5'!$B$6:$B$20,$A74,'S5'!$E$6:$E$20,"Ambos")+COUNTIFS('S6'!$B$6:$B$17,$A74,'S6'!$E$6:$E$17,"Diego")+COUNTIFS('S6'!$B$6:$B$17,$A74,'S6'!$E$6:$E$17,"Ambos")+COUNTIFS('S7'!$B$6:$B$19,$A74,'S7'!$E$6:$E$19,"Diego")+COUNTIFS('S7'!$B$6:$B$19,$A74,'S7'!$E$6:$E$19,"Ambos")+COUNTIFS('S8'!$B$6:$B$23,$A74,'S8'!$E$6:$E$23,"Diego")+COUNTIFS('S8'!$B$6:$B$23,$A74,'S8'!$E$6:$E$23,"Ambos")+COUNTIFS('S9'!$B$6:$B$15,$A74,'S9'!$E$6:$E$15,"Diego")+COUNTIFS('S9'!$B$6:$B$15,$A74,'S9'!$E$6:$E$15,"Ambos")+COUNTIFS('S10'!$B$6:$B$13,$A74,'S10'!$E$6:$E$13,"Diego")+COUNTIFS('S10'!$B$6:$B$13,$A74,'S10'!$E$6:$E$13,"Ambos")+COUNTIFS('Holgura'!$B$6:$B$11,$A74,'Holgura'!$E$6:$E$11,"Diego")+COUNTIFS('Holgura'!$B$6:$B$11,$A74,'Holgura'!$E$6:$E$11,"Ambos")+COUNTIFS('Entrega'!$B$6:$B$9,$A74,'Entrega'!$E$6:$E$9,"Diego")+COUNTIFS('Entrega'!$B$6:$B$9,$A74,'Entrega'!$E$6:$E$9,"Ambos")+COUNTIFS('Defensa'!$B$6:$B$10,$A74,'Defensa'!$E$6:$E$10,"Diego")+COUNTIFS('Defensa'!$B$6:$B$10,$A74,'Defensa'!$E$6:$E$10,"Ambos")</f>
         <v/>
       </c>
     </row>
@@ -10710,19 +10731,19 @@
         <v/>
       </c>
       <c r="D75" s="21">
-        <f>SUMIFS('S1'!$I$6:$I$32,'S1'!$B$6:$B$32,$A75,'S1'!$E$6:$E$32,"Víctor")+SUMIFS('S1'!$I$6:$I$32,'S1'!$B$6:$B$32,$A75,'S1'!$E$6:$E$32,"Ambos")+SUMIFS('S2'!$I$6:$I$23,'S2'!$B$6:$B$23,$A75,'S2'!$E$6:$E$23,"Víctor")+SUMIFS('S2'!$I$6:$I$23,'S2'!$B$6:$B$23,$A75,'S2'!$E$6:$E$23,"Ambos")+SUMIFS('S3'!$I$6:$I$19,'S3'!$B$6:$B$19,$A75,'S3'!$E$6:$E$19,"Víctor")+SUMIFS('S3'!$I$6:$I$19,'S3'!$B$6:$B$19,$A75,'S3'!$E$6:$E$19,"Ambos")+SUMIFS('S4'!$I$6:$I$20,'S4'!$B$6:$B$20,$A75,'S4'!$E$6:$E$20,"Víctor")+SUMIFS('S4'!$I$6:$I$20,'S4'!$B$6:$B$20,$A75,'S4'!$E$6:$E$20,"Ambos")+SUMIFS('S5'!$I$6:$I$20,'S5'!$B$6:$B$20,$A75,'S5'!$E$6:$E$20,"Víctor")+SUMIFS('S5'!$I$6:$I$20,'S5'!$B$6:$B$20,$A75,'S5'!$E$6:$E$20,"Ambos")+SUMIFS('S6'!$I$6:$I$17,'S6'!$B$6:$B$17,$A75,'S6'!$E$6:$E$17,"Víctor")+SUMIFS('S6'!$I$6:$I$17,'S6'!$B$6:$B$17,$A75,'S6'!$E$6:$E$17,"Ambos")+SUMIFS('S7'!$I$6:$I$19,'S7'!$B$6:$B$19,$A75,'S7'!$E$6:$E$19,"Víctor")+SUMIFS('S7'!$I$6:$I$19,'S7'!$B$6:$B$19,$A75,'S7'!$E$6:$E$19,"Ambos")+SUMIFS('S8'!$I$6:$I$23,'S8'!$B$6:$B$23,$A75,'S8'!$E$6:$E$23,"Víctor")+SUMIFS('S8'!$I$6:$I$23,'S8'!$B$6:$B$23,$A75,'S8'!$E$6:$E$23,"Ambos")+SUMIFS('S9'!$I$6:$I$15,'S9'!$B$6:$B$15,$A75,'S9'!$E$6:$E$15,"Víctor")+SUMIFS('S9'!$I$6:$I$15,'S9'!$B$6:$B$15,$A75,'S9'!$E$6:$E$15,"Ambos")+SUMIFS('S10'!$I$6:$I$13,'S10'!$B$6:$B$13,$A75,'S10'!$E$6:$E$13,"Víctor")+SUMIFS('S10'!$I$6:$I$13,'S10'!$B$6:$B$13,$A75,'S10'!$E$6:$E$13,"Ambos")+SUMIFS('Holgura'!$I$6:$I$11,'Holgura'!$B$6:$B$11,$A75,'Holgura'!$E$6:$E$11,"Víctor")+SUMIFS('Holgura'!$I$6:$I$11,'Holgura'!$B$6:$B$11,$A75,'Holgura'!$E$6:$E$11,"Ambos")+SUMIFS('Entrega'!$I$6:$I$9,'Entrega'!$B$6:$B$9,$A75,'Entrega'!$E$6:$E$9,"Víctor")+SUMIFS('Entrega'!$I$6:$I$9,'Entrega'!$B$6:$B$9,$A75,'Entrega'!$E$6:$E$9,"Ambos")+SUMIFS('Defensa'!$I$6:$I$10,'Defensa'!$B$6:$B$10,$A75,'Defensa'!$E$6:$E$10,"Víctor")+SUMIFS('Defensa'!$I$6:$I$10,'Defensa'!$B$6:$B$10,$A75,'Defensa'!$E$6:$E$10,"Ambos")</f>
+        <f>SUMIFS('S1'!$I$6:$I$32,'S1'!$B$6:$B$32,$A75,'S1'!$E$6:$E$32,"Víctor")+SUMIFS('S1'!$I$6:$I$32,'S1'!$B$6:$B$32,$A75,'S1'!$E$6:$E$32,"Ambos")+SUMIFS('S2'!$I$6:$I$23,'S2'!$B$6:$B$23,$A75,'S2'!$E$6:$E$23,"Víctor")+SUMIFS('S2'!$I$6:$I$23,'S2'!$B$6:$B$23,$A75,'S2'!$E$6:$E$23,"Ambos")+SUMIFS('S3'!$I$6:$I$24,'S3'!$B$6:$B$24,$A75,'S3'!$E$6:$E$24,"Víctor")+SUMIFS('S3'!$I$6:$I$24,'S3'!$B$6:$B$24,$A75,'S3'!$E$6:$E$24,"Ambos")+SUMIFS('S4'!$I$6:$I$22,'S4'!$B$6:$B$22,$A75,'S4'!$E$6:$E$22,"Víctor")+SUMIFS('S4'!$I$6:$I$22,'S4'!$B$6:$B$22,$A75,'S4'!$E$6:$E$22,"Ambos")+SUMIFS('S5'!$I$6:$I$20,'S5'!$B$6:$B$20,$A75,'S5'!$E$6:$E$20,"Víctor")+SUMIFS('S5'!$I$6:$I$20,'S5'!$B$6:$B$20,$A75,'S5'!$E$6:$E$20,"Ambos")+SUMIFS('S6'!$I$6:$I$17,'S6'!$B$6:$B$17,$A75,'S6'!$E$6:$E$17,"Víctor")+SUMIFS('S6'!$I$6:$I$17,'S6'!$B$6:$B$17,$A75,'S6'!$E$6:$E$17,"Ambos")+SUMIFS('S7'!$I$6:$I$19,'S7'!$B$6:$B$19,$A75,'S7'!$E$6:$E$19,"Víctor")+SUMIFS('S7'!$I$6:$I$19,'S7'!$B$6:$B$19,$A75,'S7'!$E$6:$E$19,"Ambos")+SUMIFS('S8'!$I$6:$I$23,'S8'!$B$6:$B$23,$A75,'S8'!$E$6:$E$23,"Víctor")+SUMIFS('S8'!$I$6:$I$23,'S8'!$B$6:$B$23,$A75,'S8'!$E$6:$E$23,"Ambos")+SUMIFS('S9'!$I$6:$I$15,'S9'!$B$6:$B$15,$A75,'S9'!$E$6:$E$15,"Víctor")+SUMIFS('S9'!$I$6:$I$15,'S9'!$B$6:$B$15,$A75,'S9'!$E$6:$E$15,"Ambos")+SUMIFS('S10'!$I$6:$I$13,'S10'!$B$6:$B$13,$A75,'S10'!$E$6:$E$13,"Víctor")+SUMIFS('S10'!$I$6:$I$13,'S10'!$B$6:$B$13,$A75,'S10'!$E$6:$E$13,"Ambos")+SUMIFS('Holgura'!$I$6:$I$11,'Holgura'!$B$6:$B$11,$A75,'Holgura'!$E$6:$E$11,"Víctor")+SUMIFS('Holgura'!$I$6:$I$11,'Holgura'!$B$6:$B$11,$A75,'Holgura'!$E$6:$E$11,"Ambos")+SUMIFS('Entrega'!$I$6:$I$9,'Entrega'!$B$6:$B$9,$A75,'Entrega'!$E$6:$E$9,"Víctor")+SUMIFS('Entrega'!$I$6:$I$9,'Entrega'!$B$6:$B$9,$A75,'Entrega'!$E$6:$E$9,"Ambos")+SUMIFS('Defensa'!$I$6:$I$10,'Defensa'!$B$6:$B$10,$A75,'Defensa'!$E$6:$E$10,"Víctor")+SUMIFS('Defensa'!$I$6:$I$10,'Defensa'!$B$6:$B$10,$A75,'Defensa'!$E$6:$E$10,"Ambos")</f>
         <v/>
       </c>
       <c r="E75" s="21">
-        <f>SUMIFS('S1'!$I$6:$I$32,'S1'!$B$6:$B$32,$A75,'S1'!$E$6:$E$32,"Diego")+SUMIFS('S1'!$I$6:$I$32,'S1'!$B$6:$B$32,$A75,'S1'!$E$6:$E$32,"Ambos")+SUMIFS('S2'!$I$6:$I$23,'S2'!$B$6:$B$23,$A75,'S2'!$E$6:$E$23,"Diego")+SUMIFS('S2'!$I$6:$I$23,'S2'!$B$6:$B$23,$A75,'S2'!$E$6:$E$23,"Ambos")+SUMIFS('S3'!$I$6:$I$19,'S3'!$B$6:$B$19,$A75,'S3'!$E$6:$E$19,"Diego")+SUMIFS('S3'!$I$6:$I$19,'S3'!$B$6:$B$19,$A75,'S3'!$E$6:$E$19,"Ambos")+SUMIFS('S4'!$I$6:$I$20,'S4'!$B$6:$B$20,$A75,'S4'!$E$6:$E$20,"Diego")+SUMIFS('S4'!$I$6:$I$20,'S4'!$B$6:$B$20,$A75,'S4'!$E$6:$E$20,"Ambos")+SUMIFS('S5'!$I$6:$I$20,'S5'!$B$6:$B$20,$A75,'S5'!$E$6:$E$20,"Diego")+SUMIFS('S5'!$I$6:$I$20,'S5'!$B$6:$B$20,$A75,'S5'!$E$6:$E$20,"Ambos")+SUMIFS('S6'!$I$6:$I$17,'S6'!$B$6:$B$17,$A75,'S6'!$E$6:$E$17,"Diego")+SUMIFS('S6'!$I$6:$I$17,'S6'!$B$6:$B$17,$A75,'S6'!$E$6:$E$17,"Ambos")+SUMIFS('S7'!$I$6:$I$19,'S7'!$B$6:$B$19,$A75,'S7'!$E$6:$E$19,"Diego")+SUMIFS('S7'!$I$6:$I$19,'S7'!$B$6:$B$19,$A75,'S7'!$E$6:$E$19,"Ambos")+SUMIFS('S8'!$I$6:$I$23,'S8'!$B$6:$B$23,$A75,'S8'!$E$6:$E$23,"Diego")+SUMIFS('S8'!$I$6:$I$23,'S8'!$B$6:$B$23,$A75,'S8'!$E$6:$E$23,"Ambos")+SUMIFS('S9'!$I$6:$I$15,'S9'!$B$6:$B$15,$A75,'S9'!$E$6:$E$15,"Diego")+SUMIFS('S9'!$I$6:$I$15,'S9'!$B$6:$B$15,$A75,'S9'!$E$6:$E$15,"Ambos")+SUMIFS('S10'!$I$6:$I$13,'S10'!$B$6:$B$13,$A75,'S10'!$E$6:$E$13,"Diego")+SUMIFS('S10'!$I$6:$I$13,'S10'!$B$6:$B$13,$A75,'S10'!$E$6:$E$13,"Ambos")+SUMIFS('Holgura'!$I$6:$I$11,'Holgura'!$B$6:$B$11,$A75,'Holgura'!$E$6:$E$11,"Diego")+SUMIFS('Holgura'!$I$6:$I$11,'Holgura'!$B$6:$B$11,$A75,'Holgura'!$E$6:$E$11,"Ambos")+SUMIFS('Entrega'!$I$6:$I$9,'Entrega'!$B$6:$B$9,$A75,'Entrega'!$E$6:$E$9,"Diego")+SUMIFS('Entrega'!$I$6:$I$9,'Entrega'!$B$6:$B$9,$A75,'Entrega'!$E$6:$E$9,"Ambos")+SUMIFS('Defensa'!$I$6:$I$10,'Defensa'!$B$6:$B$10,$A75,'Defensa'!$E$6:$E$10,"Diego")+SUMIFS('Defensa'!$I$6:$I$10,'Defensa'!$B$6:$B$10,$A75,'Defensa'!$E$6:$E$10,"Ambos")</f>
+        <f>SUMIFS('S1'!$I$6:$I$32,'S1'!$B$6:$B$32,$A75,'S1'!$E$6:$E$32,"Diego")+SUMIFS('S1'!$I$6:$I$32,'S1'!$B$6:$B$32,$A75,'S1'!$E$6:$E$32,"Ambos")+SUMIFS('S2'!$I$6:$I$23,'S2'!$B$6:$B$23,$A75,'S2'!$E$6:$E$23,"Diego")+SUMIFS('S2'!$I$6:$I$23,'S2'!$B$6:$B$23,$A75,'S2'!$E$6:$E$23,"Ambos")+SUMIFS('S3'!$I$6:$I$24,'S3'!$B$6:$B$24,$A75,'S3'!$E$6:$E$24,"Diego")+SUMIFS('S3'!$I$6:$I$24,'S3'!$B$6:$B$24,$A75,'S3'!$E$6:$E$24,"Ambos")+SUMIFS('S4'!$I$6:$I$22,'S4'!$B$6:$B$22,$A75,'S4'!$E$6:$E$22,"Diego")+SUMIFS('S4'!$I$6:$I$22,'S4'!$B$6:$B$22,$A75,'S4'!$E$6:$E$22,"Ambos")+SUMIFS('S5'!$I$6:$I$20,'S5'!$B$6:$B$20,$A75,'S5'!$E$6:$E$20,"Diego")+SUMIFS('S5'!$I$6:$I$20,'S5'!$B$6:$B$20,$A75,'S5'!$E$6:$E$20,"Ambos")+SUMIFS('S6'!$I$6:$I$17,'S6'!$B$6:$B$17,$A75,'S6'!$E$6:$E$17,"Diego")+SUMIFS('S6'!$I$6:$I$17,'S6'!$B$6:$B$17,$A75,'S6'!$E$6:$E$17,"Ambos")+SUMIFS('S7'!$I$6:$I$19,'S7'!$B$6:$B$19,$A75,'S7'!$E$6:$E$19,"Diego")+SUMIFS('S7'!$I$6:$I$19,'S7'!$B$6:$B$19,$A75,'S7'!$E$6:$E$19,"Ambos")+SUMIFS('S8'!$I$6:$I$23,'S8'!$B$6:$B$23,$A75,'S8'!$E$6:$E$23,"Diego")+SUMIFS('S8'!$I$6:$I$23,'S8'!$B$6:$B$23,$A75,'S8'!$E$6:$E$23,"Ambos")+SUMIFS('S9'!$I$6:$I$15,'S9'!$B$6:$B$15,$A75,'S9'!$E$6:$E$15,"Diego")+SUMIFS('S9'!$I$6:$I$15,'S9'!$B$6:$B$15,$A75,'S9'!$E$6:$E$15,"Ambos")+SUMIFS('S10'!$I$6:$I$13,'S10'!$B$6:$B$13,$A75,'S10'!$E$6:$E$13,"Diego")+SUMIFS('S10'!$I$6:$I$13,'S10'!$B$6:$B$13,$A75,'S10'!$E$6:$E$13,"Ambos")+SUMIFS('Holgura'!$I$6:$I$11,'Holgura'!$B$6:$B$11,$A75,'Holgura'!$E$6:$E$11,"Diego")+SUMIFS('Holgura'!$I$6:$I$11,'Holgura'!$B$6:$B$11,$A75,'Holgura'!$E$6:$E$11,"Ambos")+SUMIFS('Entrega'!$I$6:$I$9,'Entrega'!$B$6:$B$9,$A75,'Entrega'!$E$6:$E$9,"Diego")+SUMIFS('Entrega'!$I$6:$I$9,'Entrega'!$B$6:$B$9,$A75,'Entrega'!$E$6:$E$9,"Ambos")+SUMIFS('Defensa'!$I$6:$I$10,'Defensa'!$B$6:$B$10,$A75,'Defensa'!$E$6:$E$10,"Diego")+SUMIFS('Defensa'!$I$6:$I$10,'Defensa'!$B$6:$B$10,$A75,'Defensa'!$E$6:$E$10,"Ambos")</f>
         <v/>
       </c>
       <c r="F75" s="21">
-        <f>COUNTIFS('S1'!$B$6:$B$32,$A75,'S1'!$E$6:$E$32,"Víctor")+COUNTIFS('S1'!$B$6:$B$32,$A75,'S1'!$E$6:$E$32,"Ambos")+COUNTIFS('S2'!$B$6:$B$23,$A75,'S2'!$E$6:$E$23,"Víctor")+COUNTIFS('S2'!$B$6:$B$23,$A75,'S2'!$E$6:$E$23,"Ambos")+COUNTIFS('S3'!$B$6:$B$19,$A75,'S3'!$E$6:$E$19,"Víctor")+COUNTIFS('S3'!$B$6:$B$19,$A75,'S3'!$E$6:$E$19,"Ambos")+COUNTIFS('S4'!$B$6:$B$20,$A75,'S4'!$E$6:$E$20,"Víctor")+COUNTIFS('S4'!$B$6:$B$20,$A75,'S4'!$E$6:$E$20,"Ambos")+COUNTIFS('S5'!$B$6:$B$20,$A75,'S5'!$E$6:$E$20,"Víctor")+COUNTIFS('S5'!$B$6:$B$20,$A75,'S5'!$E$6:$E$20,"Ambos")+COUNTIFS('S6'!$B$6:$B$17,$A75,'S6'!$E$6:$E$17,"Víctor")+COUNTIFS('S6'!$B$6:$B$17,$A75,'S6'!$E$6:$E$17,"Ambos")+COUNTIFS('S7'!$B$6:$B$19,$A75,'S7'!$E$6:$E$19,"Víctor")+COUNTIFS('S7'!$B$6:$B$19,$A75,'S7'!$E$6:$E$19,"Ambos")+COUNTIFS('S8'!$B$6:$B$23,$A75,'S8'!$E$6:$E$23,"Víctor")+COUNTIFS('S8'!$B$6:$B$23,$A75,'S8'!$E$6:$E$23,"Ambos")+COUNTIFS('S9'!$B$6:$B$15,$A75,'S9'!$E$6:$E$15,"Víctor")+COUNTIFS('S9'!$B$6:$B$15,$A75,'S9'!$E$6:$E$15,"Ambos")+COUNTIFS('S10'!$B$6:$B$13,$A75,'S10'!$E$6:$E$13,"Víctor")+COUNTIFS('S10'!$B$6:$B$13,$A75,'S10'!$E$6:$E$13,"Ambos")+COUNTIFS('Holgura'!$B$6:$B$11,$A75,'Holgura'!$E$6:$E$11,"Víctor")+COUNTIFS('Holgura'!$B$6:$B$11,$A75,'Holgura'!$E$6:$E$11,"Ambos")+COUNTIFS('Entrega'!$B$6:$B$9,$A75,'Entrega'!$E$6:$E$9,"Víctor")+COUNTIFS('Entrega'!$B$6:$B$9,$A75,'Entrega'!$E$6:$E$9,"Ambos")+COUNTIFS('Defensa'!$B$6:$B$10,$A75,'Defensa'!$E$6:$E$10,"Víctor")+COUNTIFS('Defensa'!$B$6:$B$10,$A75,'Defensa'!$E$6:$E$10,"Ambos")</f>
+        <f>COUNTIFS('S1'!$B$6:$B$32,$A75,'S1'!$E$6:$E$32,"Víctor")+COUNTIFS('S1'!$B$6:$B$32,$A75,'S1'!$E$6:$E$32,"Ambos")+COUNTIFS('S2'!$B$6:$B$23,$A75,'S2'!$E$6:$E$23,"Víctor")+COUNTIFS('S2'!$B$6:$B$23,$A75,'S2'!$E$6:$E$23,"Ambos")+COUNTIFS('S3'!$B$6:$B$24,$A75,'S3'!$E$6:$E$24,"Víctor")+COUNTIFS('S3'!$B$6:$B$24,$A75,'S3'!$E$6:$E$24,"Ambos")+COUNTIFS('S4'!$B$6:$B$22,$A75,'S4'!$E$6:$E$22,"Víctor")+COUNTIFS('S4'!$B$6:$B$22,$A75,'S4'!$E$6:$E$22,"Ambos")+COUNTIFS('S5'!$B$6:$B$20,$A75,'S5'!$E$6:$E$20,"Víctor")+COUNTIFS('S5'!$B$6:$B$20,$A75,'S5'!$E$6:$E$20,"Ambos")+COUNTIFS('S6'!$B$6:$B$17,$A75,'S6'!$E$6:$E$17,"Víctor")+COUNTIFS('S6'!$B$6:$B$17,$A75,'S6'!$E$6:$E$17,"Ambos")+COUNTIFS('S7'!$B$6:$B$19,$A75,'S7'!$E$6:$E$19,"Víctor")+COUNTIFS('S7'!$B$6:$B$19,$A75,'S7'!$E$6:$E$19,"Ambos")+COUNTIFS('S8'!$B$6:$B$23,$A75,'S8'!$E$6:$E$23,"Víctor")+COUNTIFS('S8'!$B$6:$B$23,$A75,'S8'!$E$6:$E$23,"Ambos")+COUNTIFS('S9'!$B$6:$B$15,$A75,'S9'!$E$6:$E$15,"Víctor")+COUNTIFS('S9'!$B$6:$B$15,$A75,'S9'!$E$6:$E$15,"Ambos")+COUNTIFS('S10'!$B$6:$B$13,$A75,'S10'!$E$6:$E$13,"Víctor")+COUNTIFS('S10'!$B$6:$B$13,$A75,'S10'!$E$6:$E$13,"Ambos")+COUNTIFS('Holgura'!$B$6:$B$11,$A75,'Holgura'!$E$6:$E$11,"Víctor")+COUNTIFS('Holgura'!$B$6:$B$11,$A75,'Holgura'!$E$6:$E$11,"Ambos")+COUNTIFS('Entrega'!$B$6:$B$9,$A75,'Entrega'!$E$6:$E$9,"Víctor")+COUNTIFS('Entrega'!$B$6:$B$9,$A75,'Entrega'!$E$6:$E$9,"Ambos")+COUNTIFS('Defensa'!$B$6:$B$10,$A75,'Defensa'!$E$6:$E$10,"Víctor")+COUNTIFS('Defensa'!$B$6:$B$10,$A75,'Defensa'!$E$6:$E$10,"Ambos")</f>
         <v/>
       </c>
       <c r="G75" s="21">
-        <f>COUNTIFS('S1'!$B$6:$B$32,$A75,'S1'!$E$6:$E$32,"Diego")+COUNTIFS('S1'!$B$6:$B$32,$A75,'S1'!$E$6:$E$32,"Ambos")+COUNTIFS('S2'!$B$6:$B$23,$A75,'S2'!$E$6:$E$23,"Diego")+COUNTIFS('S2'!$B$6:$B$23,$A75,'S2'!$E$6:$E$23,"Ambos")+COUNTIFS('S3'!$B$6:$B$19,$A75,'S3'!$E$6:$E$19,"Diego")+COUNTIFS('S3'!$B$6:$B$19,$A75,'S3'!$E$6:$E$19,"Ambos")+COUNTIFS('S4'!$B$6:$B$20,$A75,'S4'!$E$6:$E$20,"Diego")+COUNTIFS('S4'!$B$6:$B$20,$A75,'S4'!$E$6:$E$20,"Ambos")+COUNTIFS('S5'!$B$6:$B$20,$A75,'S5'!$E$6:$E$20,"Diego")+COUNTIFS('S5'!$B$6:$B$20,$A75,'S5'!$E$6:$E$20,"Ambos")+COUNTIFS('S6'!$B$6:$B$17,$A75,'S6'!$E$6:$E$17,"Diego")+COUNTIFS('S6'!$B$6:$B$17,$A75,'S6'!$E$6:$E$17,"Ambos")+COUNTIFS('S7'!$B$6:$B$19,$A75,'S7'!$E$6:$E$19,"Diego")+COUNTIFS('S7'!$B$6:$B$19,$A75,'S7'!$E$6:$E$19,"Ambos")+COUNTIFS('S8'!$B$6:$B$23,$A75,'S8'!$E$6:$E$23,"Diego")+COUNTIFS('S8'!$B$6:$B$23,$A75,'S8'!$E$6:$E$23,"Ambos")+COUNTIFS('S9'!$B$6:$B$15,$A75,'S9'!$E$6:$E$15,"Diego")+COUNTIFS('S9'!$B$6:$B$15,$A75,'S9'!$E$6:$E$15,"Ambos")+COUNTIFS('S10'!$B$6:$B$13,$A75,'S10'!$E$6:$E$13,"Diego")+COUNTIFS('S10'!$B$6:$B$13,$A75,'S10'!$E$6:$E$13,"Ambos")+COUNTIFS('Holgura'!$B$6:$B$11,$A75,'Holgura'!$E$6:$E$11,"Diego")+COUNTIFS('Holgura'!$B$6:$B$11,$A75,'Holgura'!$E$6:$E$11,"Ambos")+COUNTIFS('Entrega'!$B$6:$B$9,$A75,'Entrega'!$E$6:$E$9,"Diego")+COUNTIFS('Entrega'!$B$6:$B$9,$A75,'Entrega'!$E$6:$E$9,"Ambos")+COUNTIFS('Defensa'!$B$6:$B$10,$A75,'Defensa'!$E$6:$E$10,"Diego")+COUNTIFS('Defensa'!$B$6:$B$10,$A75,'Defensa'!$E$6:$E$10,"Ambos")</f>
+        <f>COUNTIFS('S1'!$B$6:$B$32,$A75,'S1'!$E$6:$E$32,"Diego")+COUNTIFS('S1'!$B$6:$B$32,$A75,'S1'!$E$6:$E$32,"Ambos")+COUNTIFS('S2'!$B$6:$B$23,$A75,'S2'!$E$6:$E$23,"Diego")+COUNTIFS('S2'!$B$6:$B$23,$A75,'S2'!$E$6:$E$23,"Ambos")+COUNTIFS('S3'!$B$6:$B$24,$A75,'S3'!$E$6:$E$24,"Diego")+COUNTIFS('S3'!$B$6:$B$24,$A75,'S3'!$E$6:$E$24,"Ambos")+COUNTIFS('S4'!$B$6:$B$22,$A75,'S4'!$E$6:$E$22,"Diego")+COUNTIFS('S4'!$B$6:$B$22,$A75,'S4'!$E$6:$E$22,"Ambos")+COUNTIFS('S5'!$B$6:$B$20,$A75,'S5'!$E$6:$E$20,"Diego")+COUNTIFS('S5'!$B$6:$B$20,$A75,'S5'!$E$6:$E$20,"Ambos")+COUNTIFS('S6'!$B$6:$B$17,$A75,'S6'!$E$6:$E$17,"Diego")+COUNTIFS('S6'!$B$6:$B$17,$A75,'S6'!$E$6:$E$17,"Ambos")+COUNTIFS('S7'!$B$6:$B$19,$A75,'S7'!$E$6:$E$19,"Diego")+COUNTIFS('S7'!$B$6:$B$19,$A75,'S7'!$E$6:$E$19,"Ambos")+COUNTIFS('S8'!$B$6:$B$23,$A75,'S8'!$E$6:$E$23,"Diego")+COUNTIFS('S8'!$B$6:$B$23,$A75,'S8'!$E$6:$E$23,"Ambos")+COUNTIFS('S9'!$B$6:$B$15,$A75,'S9'!$E$6:$E$15,"Diego")+COUNTIFS('S9'!$B$6:$B$15,$A75,'S9'!$E$6:$E$15,"Ambos")+COUNTIFS('S10'!$B$6:$B$13,$A75,'S10'!$E$6:$E$13,"Diego")+COUNTIFS('S10'!$B$6:$B$13,$A75,'S10'!$E$6:$E$13,"Ambos")+COUNTIFS('Holgura'!$B$6:$B$11,$A75,'Holgura'!$E$6:$E$11,"Diego")+COUNTIFS('Holgura'!$B$6:$B$11,$A75,'Holgura'!$E$6:$E$11,"Ambos")+COUNTIFS('Entrega'!$B$6:$B$9,$A75,'Entrega'!$E$6:$E$9,"Diego")+COUNTIFS('Entrega'!$B$6:$B$9,$A75,'Entrega'!$E$6:$E$9,"Ambos")+COUNTIFS('Defensa'!$B$6:$B$10,$A75,'Defensa'!$E$6:$E$10,"Diego")+COUNTIFS('Defensa'!$B$6:$B$10,$A75,'Defensa'!$E$6:$E$10,"Ambos")</f>
         <v/>
       </c>
     </row>
@@ -10739,19 +10760,19 @@
         <v/>
       </c>
       <c r="D76" s="21">
-        <f>SUMIFS('S1'!$I$6:$I$32,'S1'!$B$6:$B$32,$A76,'S1'!$E$6:$E$32,"Víctor")+SUMIFS('S1'!$I$6:$I$32,'S1'!$B$6:$B$32,$A76,'S1'!$E$6:$E$32,"Ambos")+SUMIFS('S2'!$I$6:$I$23,'S2'!$B$6:$B$23,$A76,'S2'!$E$6:$E$23,"Víctor")+SUMIFS('S2'!$I$6:$I$23,'S2'!$B$6:$B$23,$A76,'S2'!$E$6:$E$23,"Ambos")+SUMIFS('S3'!$I$6:$I$19,'S3'!$B$6:$B$19,$A76,'S3'!$E$6:$E$19,"Víctor")+SUMIFS('S3'!$I$6:$I$19,'S3'!$B$6:$B$19,$A76,'S3'!$E$6:$E$19,"Ambos")+SUMIFS('S4'!$I$6:$I$20,'S4'!$B$6:$B$20,$A76,'S4'!$E$6:$E$20,"Víctor")+SUMIFS('S4'!$I$6:$I$20,'S4'!$B$6:$B$20,$A76,'S4'!$E$6:$E$20,"Ambos")+SUMIFS('S5'!$I$6:$I$20,'S5'!$B$6:$B$20,$A76,'S5'!$E$6:$E$20,"Víctor")+SUMIFS('S5'!$I$6:$I$20,'S5'!$B$6:$B$20,$A76,'S5'!$E$6:$E$20,"Ambos")+SUMIFS('S6'!$I$6:$I$17,'S6'!$B$6:$B$17,$A76,'S6'!$E$6:$E$17,"Víctor")+SUMIFS('S6'!$I$6:$I$17,'S6'!$B$6:$B$17,$A76,'S6'!$E$6:$E$17,"Ambos")+SUMIFS('S7'!$I$6:$I$19,'S7'!$B$6:$B$19,$A76,'S7'!$E$6:$E$19,"Víctor")+SUMIFS('S7'!$I$6:$I$19,'S7'!$B$6:$B$19,$A76,'S7'!$E$6:$E$19,"Ambos")+SUMIFS('S8'!$I$6:$I$23,'S8'!$B$6:$B$23,$A76,'S8'!$E$6:$E$23,"Víctor")+SUMIFS('S8'!$I$6:$I$23,'S8'!$B$6:$B$23,$A76,'S8'!$E$6:$E$23,"Ambos")+SUMIFS('S9'!$I$6:$I$15,'S9'!$B$6:$B$15,$A76,'S9'!$E$6:$E$15,"Víctor")+SUMIFS('S9'!$I$6:$I$15,'S9'!$B$6:$B$15,$A76,'S9'!$E$6:$E$15,"Ambos")+SUMIFS('S10'!$I$6:$I$13,'S10'!$B$6:$B$13,$A76,'S10'!$E$6:$E$13,"Víctor")+SUMIFS('S10'!$I$6:$I$13,'S10'!$B$6:$B$13,$A76,'S10'!$E$6:$E$13,"Ambos")+SUMIFS('Holgura'!$I$6:$I$11,'Holgura'!$B$6:$B$11,$A76,'Holgura'!$E$6:$E$11,"Víctor")+SUMIFS('Holgura'!$I$6:$I$11,'Holgura'!$B$6:$B$11,$A76,'Holgura'!$E$6:$E$11,"Ambos")+SUMIFS('Entrega'!$I$6:$I$9,'Entrega'!$B$6:$B$9,$A76,'Entrega'!$E$6:$E$9,"Víctor")+SUMIFS('Entrega'!$I$6:$I$9,'Entrega'!$B$6:$B$9,$A76,'Entrega'!$E$6:$E$9,"Ambos")+SUMIFS('Defensa'!$I$6:$I$10,'Defensa'!$B$6:$B$10,$A76,'Defensa'!$E$6:$E$10,"Víctor")+SUMIFS('Defensa'!$I$6:$I$10,'Defensa'!$B$6:$B$10,$A76,'Defensa'!$E$6:$E$10,"Ambos")</f>
+        <f>SUMIFS('S1'!$I$6:$I$32,'S1'!$B$6:$B$32,$A76,'S1'!$E$6:$E$32,"Víctor")+SUMIFS('S1'!$I$6:$I$32,'S1'!$B$6:$B$32,$A76,'S1'!$E$6:$E$32,"Ambos")+SUMIFS('S2'!$I$6:$I$23,'S2'!$B$6:$B$23,$A76,'S2'!$E$6:$E$23,"Víctor")+SUMIFS('S2'!$I$6:$I$23,'S2'!$B$6:$B$23,$A76,'S2'!$E$6:$E$23,"Ambos")+SUMIFS('S3'!$I$6:$I$24,'S3'!$B$6:$B$24,$A76,'S3'!$E$6:$E$24,"Víctor")+SUMIFS('S3'!$I$6:$I$24,'S3'!$B$6:$B$24,$A76,'S3'!$E$6:$E$24,"Ambos")+SUMIFS('S4'!$I$6:$I$22,'S4'!$B$6:$B$22,$A76,'S4'!$E$6:$E$22,"Víctor")+SUMIFS('S4'!$I$6:$I$22,'S4'!$B$6:$B$22,$A76,'S4'!$E$6:$E$22,"Ambos")+SUMIFS('S5'!$I$6:$I$20,'S5'!$B$6:$B$20,$A76,'S5'!$E$6:$E$20,"Víctor")+SUMIFS('S5'!$I$6:$I$20,'S5'!$B$6:$B$20,$A76,'S5'!$E$6:$E$20,"Ambos")+SUMIFS('S6'!$I$6:$I$17,'S6'!$B$6:$B$17,$A76,'S6'!$E$6:$E$17,"Víctor")+SUMIFS('S6'!$I$6:$I$17,'S6'!$B$6:$B$17,$A76,'S6'!$E$6:$E$17,"Ambos")+SUMIFS('S7'!$I$6:$I$19,'S7'!$B$6:$B$19,$A76,'S7'!$E$6:$E$19,"Víctor")+SUMIFS('S7'!$I$6:$I$19,'S7'!$B$6:$B$19,$A76,'S7'!$E$6:$E$19,"Ambos")+SUMIFS('S8'!$I$6:$I$23,'S8'!$B$6:$B$23,$A76,'S8'!$E$6:$E$23,"Víctor")+SUMIFS('S8'!$I$6:$I$23,'S8'!$B$6:$B$23,$A76,'S8'!$E$6:$E$23,"Ambos")+SUMIFS('S9'!$I$6:$I$15,'S9'!$B$6:$B$15,$A76,'S9'!$E$6:$E$15,"Víctor")+SUMIFS('S9'!$I$6:$I$15,'S9'!$B$6:$B$15,$A76,'S9'!$E$6:$E$15,"Ambos")+SUMIFS('S10'!$I$6:$I$13,'S10'!$B$6:$B$13,$A76,'S10'!$E$6:$E$13,"Víctor")+SUMIFS('S10'!$I$6:$I$13,'S10'!$B$6:$B$13,$A76,'S10'!$E$6:$E$13,"Ambos")+SUMIFS('Holgura'!$I$6:$I$11,'Holgura'!$B$6:$B$11,$A76,'Holgura'!$E$6:$E$11,"Víctor")+SUMIFS('Holgura'!$I$6:$I$11,'Holgura'!$B$6:$B$11,$A76,'Holgura'!$E$6:$E$11,"Ambos")+SUMIFS('Entrega'!$I$6:$I$9,'Entrega'!$B$6:$B$9,$A76,'Entrega'!$E$6:$E$9,"Víctor")+SUMIFS('Entrega'!$I$6:$I$9,'Entrega'!$B$6:$B$9,$A76,'Entrega'!$E$6:$E$9,"Ambos")+SUMIFS('Defensa'!$I$6:$I$10,'Defensa'!$B$6:$B$10,$A76,'Defensa'!$E$6:$E$10,"Víctor")+SUMIFS('Defensa'!$I$6:$I$10,'Defensa'!$B$6:$B$10,$A76,'Defensa'!$E$6:$E$10,"Ambos")</f>
         <v/>
       </c>
       <c r="E76" s="21">
-        <f>SUMIFS('S1'!$I$6:$I$32,'S1'!$B$6:$B$32,$A76,'S1'!$E$6:$E$32,"Diego")+SUMIFS('S1'!$I$6:$I$32,'S1'!$B$6:$B$32,$A76,'S1'!$E$6:$E$32,"Ambos")+SUMIFS('S2'!$I$6:$I$23,'S2'!$B$6:$B$23,$A76,'S2'!$E$6:$E$23,"Diego")+SUMIFS('S2'!$I$6:$I$23,'S2'!$B$6:$B$23,$A76,'S2'!$E$6:$E$23,"Ambos")+SUMIFS('S3'!$I$6:$I$19,'S3'!$B$6:$B$19,$A76,'S3'!$E$6:$E$19,"Diego")+SUMIFS('S3'!$I$6:$I$19,'S3'!$B$6:$B$19,$A76,'S3'!$E$6:$E$19,"Ambos")+SUMIFS('S4'!$I$6:$I$20,'S4'!$B$6:$B$20,$A76,'S4'!$E$6:$E$20,"Diego")+SUMIFS('S4'!$I$6:$I$20,'S4'!$B$6:$B$20,$A76,'S4'!$E$6:$E$20,"Ambos")+SUMIFS('S5'!$I$6:$I$20,'S5'!$B$6:$B$20,$A76,'S5'!$E$6:$E$20,"Diego")+SUMIFS('S5'!$I$6:$I$20,'S5'!$B$6:$B$20,$A76,'S5'!$E$6:$E$20,"Ambos")+SUMIFS('S6'!$I$6:$I$17,'S6'!$B$6:$B$17,$A76,'S6'!$E$6:$E$17,"Diego")+SUMIFS('S6'!$I$6:$I$17,'S6'!$B$6:$B$17,$A76,'S6'!$E$6:$E$17,"Ambos")+SUMIFS('S7'!$I$6:$I$19,'S7'!$B$6:$B$19,$A76,'S7'!$E$6:$E$19,"Diego")+SUMIFS('S7'!$I$6:$I$19,'S7'!$B$6:$B$19,$A76,'S7'!$E$6:$E$19,"Ambos")+SUMIFS('S8'!$I$6:$I$23,'S8'!$B$6:$B$23,$A76,'S8'!$E$6:$E$23,"Diego")+SUMIFS('S8'!$I$6:$I$23,'S8'!$B$6:$B$23,$A76,'S8'!$E$6:$E$23,"Ambos")+SUMIFS('S9'!$I$6:$I$15,'S9'!$B$6:$B$15,$A76,'S9'!$E$6:$E$15,"Diego")+SUMIFS('S9'!$I$6:$I$15,'S9'!$B$6:$B$15,$A76,'S9'!$E$6:$E$15,"Ambos")+SUMIFS('S10'!$I$6:$I$13,'S10'!$B$6:$B$13,$A76,'S10'!$E$6:$E$13,"Diego")+SUMIFS('S10'!$I$6:$I$13,'S10'!$B$6:$B$13,$A76,'S10'!$E$6:$E$13,"Ambos")+SUMIFS('Holgura'!$I$6:$I$11,'Holgura'!$B$6:$B$11,$A76,'Holgura'!$E$6:$E$11,"Diego")+SUMIFS('Holgura'!$I$6:$I$11,'Holgura'!$B$6:$B$11,$A76,'Holgura'!$E$6:$E$11,"Ambos")+SUMIFS('Entrega'!$I$6:$I$9,'Entrega'!$B$6:$B$9,$A76,'Entrega'!$E$6:$E$9,"Diego")+SUMIFS('Entrega'!$I$6:$I$9,'Entrega'!$B$6:$B$9,$A76,'Entrega'!$E$6:$E$9,"Ambos")+SUMIFS('Defensa'!$I$6:$I$10,'Defensa'!$B$6:$B$10,$A76,'Defensa'!$E$6:$E$10,"Diego")+SUMIFS('Defensa'!$I$6:$I$10,'Defensa'!$B$6:$B$10,$A76,'Defensa'!$E$6:$E$10,"Ambos")</f>
+        <f>SUMIFS('S1'!$I$6:$I$32,'S1'!$B$6:$B$32,$A76,'S1'!$E$6:$E$32,"Diego")+SUMIFS('S1'!$I$6:$I$32,'S1'!$B$6:$B$32,$A76,'S1'!$E$6:$E$32,"Ambos")+SUMIFS('S2'!$I$6:$I$23,'S2'!$B$6:$B$23,$A76,'S2'!$E$6:$E$23,"Diego")+SUMIFS('S2'!$I$6:$I$23,'S2'!$B$6:$B$23,$A76,'S2'!$E$6:$E$23,"Ambos")+SUMIFS('S3'!$I$6:$I$24,'S3'!$B$6:$B$24,$A76,'S3'!$E$6:$E$24,"Diego")+SUMIFS('S3'!$I$6:$I$24,'S3'!$B$6:$B$24,$A76,'S3'!$E$6:$E$24,"Ambos")+SUMIFS('S4'!$I$6:$I$22,'S4'!$B$6:$B$22,$A76,'S4'!$E$6:$E$22,"Diego")+SUMIFS('S4'!$I$6:$I$22,'S4'!$B$6:$B$22,$A76,'S4'!$E$6:$E$22,"Ambos")+SUMIFS('S5'!$I$6:$I$20,'S5'!$B$6:$B$20,$A76,'S5'!$E$6:$E$20,"Diego")+SUMIFS('S5'!$I$6:$I$20,'S5'!$B$6:$B$20,$A76,'S5'!$E$6:$E$20,"Ambos")+SUMIFS('S6'!$I$6:$I$17,'S6'!$B$6:$B$17,$A76,'S6'!$E$6:$E$17,"Diego")+SUMIFS('S6'!$I$6:$I$17,'S6'!$B$6:$B$17,$A76,'S6'!$E$6:$E$17,"Ambos")+SUMIFS('S7'!$I$6:$I$19,'S7'!$B$6:$B$19,$A76,'S7'!$E$6:$E$19,"Diego")+SUMIFS('S7'!$I$6:$I$19,'S7'!$B$6:$B$19,$A76,'S7'!$E$6:$E$19,"Ambos")+SUMIFS('S8'!$I$6:$I$23,'S8'!$B$6:$B$23,$A76,'S8'!$E$6:$E$23,"Diego")+SUMIFS('S8'!$I$6:$I$23,'S8'!$B$6:$B$23,$A76,'S8'!$E$6:$E$23,"Ambos")+SUMIFS('S9'!$I$6:$I$15,'S9'!$B$6:$B$15,$A76,'S9'!$E$6:$E$15,"Diego")+SUMIFS('S9'!$I$6:$I$15,'S9'!$B$6:$B$15,$A76,'S9'!$E$6:$E$15,"Ambos")+SUMIFS('S10'!$I$6:$I$13,'S10'!$B$6:$B$13,$A76,'S10'!$E$6:$E$13,"Diego")+SUMIFS('S10'!$I$6:$I$13,'S10'!$B$6:$B$13,$A76,'S10'!$E$6:$E$13,"Ambos")+SUMIFS('Holgura'!$I$6:$I$11,'Holgura'!$B$6:$B$11,$A76,'Holgura'!$E$6:$E$11,"Diego")+SUMIFS('Holgura'!$I$6:$I$11,'Holgura'!$B$6:$B$11,$A76,'Holgura'!$E$6:$E$11,"Ambos")+SUMIFS('Entrega'!$I$6:$I$9,'Entrega'!$B$6:$B$9,$A76,'Entrega'!$E$6:$E$9,"Diego")+SUMIFS('Entrega'!$I$6:$I$9,'Entrega'!$B$6:$B$9,$A76,'Entrega'!$E$6:$E$9,"Ambos")+SUMIFS('Defensa'!$I$6:$I$10,'Defensa'!$B$6:$B$10,$A76,'Defensa'!$E$6:$E$10,"Diego")+SUMIFS('Defensa'!$I$6:$I$10,'Defensa'!$B$6:$B$10,$A76,'Defensa'!$E$6:$E$10,"Ambos")</f>
         <v/>
       </c>
       <c r="F76" s="21">
-        <f>COUNTIFS('S1'!$B$6:$B$32,$A76,'S1'!$E$6:$E$32,"Víctor")+COUNTIFS('S1'!$B$6:$B$32,$A76,'S1'!$E$6:$E$32,"Ambos")+COUNTIFS('S2'!$B$6:$B$23,$A76,'S2'!$E$6:$E$23,"Víctor")+COUNTIFS('S2'!$B$6:$B$23,$A76,'S2'!$E$6:$E$23,"Ambos")+COUNTIFS('S3'!$B$6:$B$19,$A76,'S3'!$E$6:$E$19,"Víctor")+COUNTIFS('S3'!$B$6:$B$19,$A76,'S3'!$E$6:$E$19,"Ambos")+COUNTIFS('S4'!$B$6:$B$20,$A76,'S4'!$E$6:$E$20,"Víctor")+COUNTIFS('S4'!$B$6:$B$20,$A76,'S4'!$E$6:$E$20,"Ambos")+COUNTIFS('S5'!$B$6:$B$20,$A76,'S5'!$E$6:$E$20,"Víctor")+COUNTIFS('S5'!$B$6:$B$20,$A76,'S5'!$E$6:$E$20,"Ambos")+COUNTIFS('S6'!$B$6:$B$17,$A76,'S6'!$E$6:$E$17,"Víctor")+COUNTIFS('S6'!$B$6:$B$17,$A76,'S6'!$E$6:$E$17,"Ambos")+COUNTIFS('S7'!$B$6:$B$19,$A76,'S7'!$E$6:$E$19,"Víctor")+COUNTIFS('S7'!$B$6:$B$19,$A76,'S7'!$E$6:$E$19,"Ambos")+COUNTIFS('S8'!$B$6:$B$23,$A76,'S8'!$E$6:$E$23,"Víctor")+COUNTIFS('S8'!$B$6:$B$23,$A76,'S8'!$E$6:$E$23,"Ambos")+COUNTIFS('S9'!$B$6:$B$15,$A76,'S9'!$E$6:$E$15,"Víctor")+COUNTIFS('S9'!$B$6:$B$15,$A76,'S9'!$E$6:$E$15,"Ambos")+COUNTIFS('S10'!$B$6:$B$13,$A76,'S10'!$E$6:$E$13,"Víctor")+COUNTIFS('S10'!$B$6:$B$13,$A76,'S10'!$E$6:$E$13,"Ambos")+COUNTIFS('Holgura'!$B$6:$B$11,$A76,'Holgura'!$E$6:$E$11,"Víctor")+COUNTIFS('Holgura'!$B$6:$B$11,$A76,'Holgura'!$E$6:$E$11,"Ambos")+COUNTIFS('Entrega'!$B$6:$B$9,$A76,'Entrega'!$E$6:$E$9,"Víctor")+COUNTIFS('Entrega'!$B$6:$B$9,$A76,'Entrega'!$E$6:$E$9,"Ambos")+COUNTIFS('Defensa'!$B$6:$B$10,$A76,'Defensa'!$E$6:$E$10,"Víctor")+COUNTIFS('Defensa'!$B$6:$B$10,$A76,'Defensa'!$E$6:$E$10,"Ambos")</f>
+        <f>COUNTIFS('S1'!$B$6:$B$32,$A76,'S1'!$E$6:$E$32,"Víctor")+COUNTIFS('S1'!$B$6:$B$32,$A76,'S1'!$E$6:$E$32,"Ambos")+COUNTIFS('S2'!$B$6:$B$23,$A76,'S2'!$E$6:$E$23,"Víctor")+COUNTIFS('S2'!$B$6:$B$23,$A76,'S2'!$E$6:$E$23,"Ambos")+COUNTIFS('S3'!$B$6:$B$24,$A76,'S3'!$E$6:$E$24,"Víctor")+COUNTIFS('S3'!$B$6:$B$24,$A76,'S3'!$E$6:$E$24,"Ambos")+COUNTIFS('S4'!$B$6:$B$22,$A76,'S4'!$E$6:$E$22,"Víctor")+COUNTIFS('S4'!$B$6:$B$22,$A76,'S4'!$E$6:$E$22,"Ambos")+COUNTIFS('S5'!$B$6:$B$20,$A76,'S5'!$E$6:$E$20,"Víctor")+COUNTIFS('S5'!$B$6:$B$20,$A76,'S5'!$E$6:$E$20,"Ambos")+COUNTIFS('S6'!$B$6:$B$17,$A76,'S6'!$E$6:$E$17,"Víctor")+COUNTIFS('S6'!$B$6:$B$17,$A76,'S6'!$E$6:$E$17,"Ambos")+COUNTIFS('S7'!$B$6:$B$19,$A76,'S7'!$E$6:$E$19,"Víctor")+COUNTIFS('S7'!$B$6:$B$19,$A76,'S7'!$E$6:$E$19,"Ambos")+COUNTIFS('S8'!$B$6:$B$23,$A76,'S8'!$E$6:$E$23,"Víctor")+COUNTIFS('S8'!$B$6:$B$23,$A76,'S8'!$E$6:$E$23,"Ambos")+COUNTIFS('S9'!$B$6:$B$15,$A76,'S9'!$E$6:$E$15,"Víctor")+COUNTIFS('S9'!$B$6:$B$15,$A76,'S9'!$E$6:$E$15,"Ambos")+COUNTIFS('S10'!$B$6:$B$13,$A76,'S10'!$E$6:$E$13,"Víctor")+COUNTIFS('S10'!$B$6:$B$13,$A76,'S10'!$E$6:$E$13,"Ambos")+COUNTIFS('Holgura'!$B$6:$B$11,$A76,'Holgura'!$E$6:$E$11,"Víctor")+COUNTIFS('Holgura'!$B$6:$B$11,$A76,'Holgura'!$E$6:$E$11,"Ambos")+COUNTIFS('Entrega'!$B$6:$B$9,$A76,'Entrega'!$E$6:$E$9,"Víctor")+COUNTIFS('Entrega'!$B$6:$B$9,$A76,'Entrega'!$E$6:$E$9,"Ambos")+COUNTIFS('Defensa'!$B$6:$B$10,$A76,'Defensa'!$E$6:$E$10,"Víctor")+COUNTIFS('Defensa'!$B$6:$B$10,$A76,'Defensa'!$E$6:$E$10,"Ambos")</f>
         <v/>
       </c>
       <c r="G76" s="21">
-        <f>COUNTIFS('S1'!$B$6:$B$32,$A76,'S1'!$E$6:$E$32,"Diego")+COUNTIFS('S1'!$B$6:$B$32,$A76,'S1'!$E$6:$E$32,"Ambos")+COUNTIFS('S2'!$B$6:$B$23,$A76,'S2'!$E$6:$E$23,"Diego")+COUNTIFS('S2'!$B$6:$B$23,$A76,'S2'!$E$6:$E$23,"Ambos")+COUNTIFS('S3'!$B$6:$B$19,$A76,'S3'!$E$6:$E$19,"Diego")+COUNTIFS('S3'!$B$6:$B$19,$A76,'S3'!$E$6:$E$19,"Ambos")+COUNTIFS('S4'!$B$6:$B$20,$A76,'S4'!$E$6:$E$20,"Diego")+COUNTIFS('S4'!$B$6:$B$20,$A76,'S4'!$E$6:$E$20,"Ambos")+COUNTIFS('S5'!$B$6:$B$20,$A76,'S5'!$E$6:$E$20,"Diego")+COUNTIFS('S5'!$B$6:$B$20,$A76,'S5'!$E$6:$E$20,"Ambos")+COUNTIFS('S6'!$B$6:$B$17,$A76,'S6'!$E$6:$E$17,"Diego")+COUNTIFS('S6'!$B$6:$B$17,$A76,'S6'!$E$6:$E$17,"Ambos")+COUNTIFS('S7'!$B$6:$B$19,$A76,'S7'!$E$6:$E$19,"Diego")+COUNTIFS('S7'!$B$6:$B$19,$A76,'S7'!$E$6:$E$19,"Ambos")+COUNTIFS('S8'!$B$6:$B$23,$A76,'S8'!$E$6:$E$23,"Diego")+COUNTIFS('S8'!$B$6:$B$23,$A76,'S8'!$E$6:$E$23,"Ambos")+COUNTIFS('S9'!$B$6:$B$15,$A76,'S9'!$E$6:$E$15,"Diego")+COUNTIFS('S9'!$B$6:$B$15,$A76,'S9'!$E$6:$E$15,"Ambos")+COUNTIFS('S10'!$B$6:$B$13,$A76,'S10'!$E$6:$E$13,"Diego")+COUNTIFS('S10'!$B$6:$B$13,$A76,'S10'!$E$6:$E$13,"Ambos")+COUNTIFS('Holgura'!$B$6:$B$11,$A76,'Holgura'!$E$6:$E$11,"Diego")+COUNTIFS('Holgura'!$B$6:$B$11,$A76,'Holgura'!$E$6:$E$11,"Ambos")+COUNTIFS('Entrega'!$B$6:$B$9,$A76,'Entrega'!$E$6:$E$9,"Diego")+COUNTIFS('Entrega'!$B$6:$B$9,$A76,'Entrega'!$E$6:$E$9,"Ambos")+COUNTIFS('Defensa'!$B$6:$B$10,$A76,'Defensa'!$E$6:$E$10,"Diego")+COUNTIFS('Defensa'!$B$6:$B$10,$A76,'Defensa'!$E$6:$E$10,"Ambos")</f>
+        <f>COUNTIFS('S1'!$B$6:$B$32,$A76,'S1'!$E$6:$E$32,"Diego")+COUNTIFS('S1'!$B$6:$B$32,$A76,'S1'!$E$6:$E$32,"Ambos")+COUNTIFS('S2'!$B$6:$B$23,$A76,'S2'!$E$6:$E$23,"Diego")+COUNTIFS('S2'!$B$6:$B$23,$A76,'S2'!$E$6:$E$23,"Ambos")+COUNTIFS('S3'!$B$6:$B$24,$A76,'S3'!$E$6:$E$24,"Diego")+COUNTIFS('S3'!$B$6:$B$24,$A76,'S3'!$E$6:$E$24,"Ambos")+COUNTIFS('S4'!$B$6:$B$22,$A76,'S4'!$E$6:$E$22,"Diego")+COUNTIFS('S4'!$B$6:$B$22,$A76,'S4'!$E$6:$E$22,"Ambos")+COUNTIFS('S5'!$B$6:$B$20,$A76,'S5'!$E$6:$E$20,"Diego")+COUNTIFS('S5'!$B$6:$B$20,$A76,'S5'!$E$6:$E$20,"Ambos")+COUNTIFS('S6'!$B$6:$B$17,$A76,'S6'!$E$6:$E$17,"Diego")+COUNTIFS('S6'!$B$6:$B$17,$A76,'S6'!$E$6:$E$17,"Ambos")+COUNTIFS('S7'!$B$6:$B$19,$A76,'S7'!$E$6:$E$19,"Diego")+COUNTIFS('S7'!$B$6:$B$19,$A76,'S7'!$E$6:$E$19,"Ambos")+COUNTIFS('S8'!$B$6:$B$23,$A76,'S8'!$E$6:$E$23,"Diego")+COUNTIFS('S8'!$B$6:$B$23,$A76,'S8'!$E$6:$E$23,"Ambos")+COUNTIFS('S9'!$B$6:$B$15,$A76,'S9'!$E$6:$E$15,"Diego")+COUNTIFS('S9'!$B$6:$B$15,$A76,'S9'!$E$6:$E$15,"Ambos")+COUNTIFS('S10'!$B$6:$B$13,$A76,'S10'!$E$6:$E$13,"Diego")+COUNTIFS('S10'!$B$6:$B$13,$A76,'S10'!$E$6:$E$13,"Ambos")+COUNTIFS('Holgura'!$B$6:$B$11,$A76,'Holgura'!$E$6:$E$11,"Diego")+COUNTIFS('Holgura'!$B$6:$B$11,$A76,'Holgura'!$E$6:$E$11,"Ambos")+COUNTIFS('Entrega'!$B$6:$B$9,$A76,'Entrega'!$E$6:$E$9,"Diego")+COUNTIFS('Entrega'!$B$6:$B$9,$A76,'Entrega'!$E$6:$E$9,"Ambos")+COUNTIFS('Defensa'!$B$6:$B$10,$A76,'Defensa'!$E$6:$E$10,"Diego")+COUNTIFS('Defensa'!$B$6:$B$10,$A76,'Defensa'!$E$6:$E$10,"Ambos")</f>
         <v/>
       </c>
     </row>
@@ -10768,19 +10789,19 @@
         <v/>
       </c>
       <c r="D77" s="21">
-        <f>SUMIFS('S1'!$I$6:$I$32,'S1'!$B$6:$B$32,$A77,'S1'!$E$6:$E$32,"Víctor")+SUMIFS('S1'!$I$6:$I$32,'S1'!$B$6:$B$32,$A77,'S1'!$E$6:$E$32,"Ambos")+SUMIFS('S2'!$I$6:$I$23,'S2'!$B$6:$B$23,$A77,'S2'!$E$6:$E$23,"Víctor")+SUMIFS('S2'!$I$6:$I$23,'S2'!$B$6:$B$23,$A77,'S2'!$E$6:$E$23,"Ambos")+SUMIFS('S3'!$I$6:$I$19,'S3'!$B$6:$B$19,$A77,'S3'!$E$6:$E$19,"Víctor")+SUMIFS('S3'!$I$6:$I$19,'S3'!$B$6:$B$19,$A77,'S3'!$E$6:$E$19,"Ambos")+SUMIFS('S4'!$I$6:$I$20,'S4'!$B$6:$B$20,$A77,'S4'!$E$6:$E$20,"Víctor")+SUMIFS('S4'!$I$6:$I$20,'S4'!$B$6:$B$20,$A77,'S4'!$E$6:$E$20,"Ambos")+SUMIFS('S5'!$I$6:$I$20,'S5'!$B$6:$B$20,$A77,'S5'!$E$6:$E$20,"Víctor")+SUMIFS('S5'!$I$6:$I$20,'S5'!$B$6:$B$20,$A77,'S5'!$E$6:$E$20,"Ambos")+SUMIFS('S6'!$I$6:$I$17,'S6'!$B$6:$B$17,$A77,'S6'!$E$6:$E$17,"Víctor")+SUMIFS('S6'!$I$6:$I$17,'S6'!$B$6:$B$17,$A77,'S6'!$E$6:$E$17,"Ambos")+SUMIFS('S7'!$I$6:$I$19,'S7'!$B$6:$B$19,$A77,'S7'!$E$6:$E$19,"Víctor")+SUMIFS('S7'!$I$6:$I$19,'S7'!$B$6:$B$19,$A77,'S7'!$E$6:$E$19,"Ambos")+SUMIFS('S8'!$I$6:$I$23,'S8'!$B$6:$B$23,$A77,'S8'!$E$6:$E$23,"Víctor")+SUMIFS('S8'!$I$6:$I$23,'S8'!$B$6:$B$23,$A77,'S8'!$E$6:$E$23,"Ambos")+SUMIFS('S9'!$I$6:$I$15,'S9'!$B$6:$B$15,$A77,'S9'!$E$6:$E$15,"Víctor")+SUMIFS('S9'!$I$6:$I$15,'S9'!$B$6:$B$15,$A77,'S9'!$E$6:$E$15,"Ambos")+SUMIFS('S10'!$I$6:$I$13,'S10'!$B$6:$B$13,$A77,'S10'!$E$6:$E$13,"Víctor")+SUMIFS('S10'!$I$6:$I$13,'S10'!$B$6:$B$13,$A77,'S10'!$E$6:$E$13,"Ambos")+SUMIFS('Holgura'!$I$6:$I$11,'Holgura'!$B$6:$B$11,$A77,'Holgura'!$E$6:$E$11,"Víctor")+SUMIFS('Holgura'!$I$6:$I$11,'Holgura'!$B$6:$B$11,$A77,'Holgura'!$E$6:$E$11,"Ambos")+SUMIFS('Entrega'!$I$6:$I$9,'Entrega'!$B$6:$B$9,$A77,'Entrega'!$E$6:$E$9,"Víctor")+SUMIFS('Entrega'!$I$6:$I$9,'Entrega'!$B$6:$B$9,$A77,'Entrega'!$E$6:$E$9,"Ambos")+SUMIFS('Defensa'!$I$6:$I$10,'Defensa'!$B$6:$B$10,$A77,'Defensa'!$E$6:$E$10,"Víctor")+SUMIFS('Defensa'!$I$6:$I$10,'Defensa'!$B$6:$B$10,$A77,'Defensa'!$E$6:$E$10,"Ambos")</f>
+        <f>SUMIFS('S1'!$I$6:$I$32,'S1'!$B$6:$B$32,$A77,'S1'!$E$6:$E$32,"Víctor")+SUMIFS('S1'!$I$6:$I$32,'S1'!$B$6:$B$32,$A77,'S1'!$E$6:$E$32,"Ambos")+SUMIFS('S2'!$I$6:$I$23,'S2'!$B$6:$B$23,$A77,'S2'!$E$6:$E$23,"Víctor")+SUMIFS('S2'!$I$6:$I$23,'S2'!$B$6:$B$23,$A77,'S2'!$E$6:$E$23,"Ambos")+SUMIFS('S3'!$I$6:$I$24,'S3'!$B$6:$B$24,$A77,'S3'!$E$6:$E$24,"Víctor")+SUMIFS('S3'!$I$6:$I$24,'S3'!$B$6:$B$24,$A77,'S3'!$E$6:$E$24,"Ambos")+SUMIFS('S4'!$I$6:$I$22,'S4'!$B$6:$B$22,$A77,'S4'!$E$6:$E$22,"Víctor")+SUMIFS('S4'!$I$6:$I$22,'S4'!$B$6:$B$22,$A77,'S4'!$E$6:$E$22,"Ambos")+SUMIFS('S5'!$I$6:$I$20,'S5'!$B$6:$B$20,$A77,'S5'!$E$6:$E$20,"Víctor")+SUMIFS('S5'!$I$6:$I$20,'S5'!$B$6:$B$20,$A77,'S5'!$E$6:$E$20,"Ambos")+SUMIFS('S6'!$I$6:$I$17,'S6'!$B$6:$B$17,$A77,'S6'!$E$6:$E$17,"Víctor")+SUMIFS('S6'!$I$6:$I$17,'S6'!$B$6:$B$17,$A77,'S6'!$E$6:$E$17,"Ambos")+SUMIFS('S7'!$I$6:$I$19,'S7'!$B$6:$B$19,$A77,'S7'!$E$6:$E$19,"Víctor")+SUMIFS('S7'!$I$6:$I$19,'S7'!$B$6:$B$19,$A77,'S7'!$E$6:$E$19,"Ambos")+SUMIFS('S8'!$I$6:$I$23,'S8'!$B$6:$B$23,$A77,'S8'!$E$6:$E$23,"Víctor")+SUMIFS('S8'!$I$6:$I$23,'S8'!$B$6:$B$23,$A77,'S8'!$E$6:$E$23,"Ambos")+SUMIFS('S9'!$I$6:$I$15,'S9'!$B$6:$B$15,$A77,'S9'!$E$6:$E$15,"Víctor")+SUMIFS('S9'!$I$6:$I$15,'S9'!$B$6:$B$15,$A77,'S9'!$E$6:$E$15,"Ambos")+SUMIFS('S10'!$I$6:$I$13,'S10'!$B$6:$B$13,$A77,'S10'!$E$6:$E$13,"Víctor")+SUMIFS('S10'!$I$6:$I$13,'S10'!$B$6:$B$13,$A77,'S10'!$E$6:$E$13,"Ambos")+SUMIFS('Holgura'!$I$6:$I$11,'Holgura'!$B$6:$B$11,$A77,'Holgura'!$E$6:$E$11,"Víctor")+SUMIFS('Holgura'!$I$6:$I$11,'Holgura'!$B$6:$B$11,$A77,'Holgura'!$E$6:$E$11,"Ambos")+SUMIFS('Entrega'!$I$6:$I$9,'Entrega'!$B$6:$B$9,$A77,'Entrega'!$E$6:$E$9,"Víctor")+SUMIFS('Entrega'!$I$6:$I$9,'Entrega'!$B$6:$B$9,$A77,'Entrega'!$E$6:$E$9,"Ambos")+SUMIFS('Defensa'!$I$6:$I$10,'Defensa'!$B$6:$B$10,$A77,'Defensa'!$E$6:$E$10,"Víctor")+SUMIFS('Defensa'!$I$6:$I$10,'Defensa'!$B$6:$B$10,$A77,'Defensa'!$E$6:$E$10,"Ambos")</f>
         <v/>
       </c>
       <c r="E77" s="21">
-        <f>SUMIFS('S1'!$I$6:$I$32,'S1'!$B$6:$B$32,$A77,'S1'!$E$6:$E$32,"Diego")+SUMIFS('S1'!$I$6:$I$32,'S1'!$B$6:$B$32,$A77,'S1'!$E$6:$E$32,"Ambos")+SUMIFS('S2'!$I$6:$I$23,'S2'!$B$6:$B$23,$A77,'S2'!$E$6:$E$23,"Diego")+SUMIFS('S2'!$I$6:$I$23,'S2'!$B$6:$B$23,$A77,'S2'!$E$6:$E$23,"Ambos")+SUMIFS('S3'!$I$6:$I$19,'S3'!$B$6:$B$19,$A77,'S3'!$E$6:$E$19,"Diego")+SUMIFS('S3'!$I$6:$I$19,'S3'!$B$6:$B$19,$A77,'S3'!$E$6:$E$19,"Ambos")+SUMIFS('S4'!$I$6:$I$20,'S4'!$B$6:$B$20,$A77,'S4'!$E$6:$E$20,"Diego")+SUMIFS('S4'!$I$6:$I$20,'S4'!$B$6:$B$20,$A77,'S4'!$E$6:$E$20,"Ambos")+SUMIFS('S5'!$I$6:$I$20,'S5'!$B$6:$B$20,$A77,'S5'!$E$6:$E$20,"Diego")+SUMIFS('S5'!$I$6:$I$20,'S5'!$B$6:$B$20,$A77,'S5'!$E$6:$E$20,"Ambos")+SUMIFS('S6'!$I$6:$I$17,'S6'!$B$6:$B$17,$A77,'S6'!$E$6:$E$17,"Diego")+SUMIFS('S6'!$I$6:$I$17,'S6'!$B$6:$B$17,$A77,'S6'!$E$6:$E$17,"Ambos")+SUMIFS('S7'!$I$6:$I$19,'S7'!$B$6:$B$19,$A77,'S7'!$E$6:$E$19,"Diego")+SUMIFS('S7'!$I$6:$I$19,'S7'!$B$6:$B$19,$A77,'S7'!$E$6:$E$19,"Ambos")+SUMIFS('S8'!$I$6:$I$23,'S8'!$B$6:$B$23,$A77,'S8'!$E$6:$E$23,"Diego")+SUMIFS('S8'!$I$6:$I$23,'S8'!$B$6:$B$23,$A77,'S8'!$E$6:$E$23,"Ambos")+SUMIFS('S9'!$I$6:$I$15,'S9'!$B$6:$B$15,$A77,'S9'!$E$6:$E$15,"Diego")+SUMIFS('S9'!$I$6:$I$15,'S9'!$B$6:$B$15,$A77,'S9'!$E$6:$E$15,"Ambos")+SUMIFS('S10'!$I$6:$I$13,'S10'!$B$6:$B$13,$A77,'S10'!$E$6:$E$13,"Diego")+SUMIFS('S10'!$I$6:$I$13,'S10'!$B$6:$B$13,$A77,'S10'!$E$6:$E$13,"Ambos")+SUMIFS('Holgura'!$I$6:$I$11,'Holgura'!$B$6:$B$11,$A77,'Holgura'!$E$6:$E$11,"Diego")+SUMIFS('Holgura'!$I$6:$I$11,'Holgura'!$B$6:$B$11,$A77,'Holgura'!$E$6:$E$11,"Ambos")+SUMIFS('Entrega'!$I$6:$I$9,'Entrega'!$B$6:$B$9,$A77,'Entrega'!$E$6:$E$9,"Diego")+SUMIFS('Entrega'!$I$6:$I$9,'Entrega'!$B$6:$B$9,$A77,'Entrega'!$E$6:$E$9,"Ambos")+SUMIFS('Defensa'!$I$6:$I$10,'Defensa'!$B$6:$B$10,$A77,'Defensa'!$E$6:$E$10,"Diego")+SUMIFS('Defensa'!$I$6:$I$10,'Defensa'!$B$6:$B$10,$A77,'Defensa'!$E$6:$E$10,"Ambos")</f>
+        <f>SUMIFS('S1'!$I$6:$I$32,'S1'!$B$6:$B$32,$A77,'S1'!$E$6:$E$32,"Diego")+SUMIFS('S1'!$I$6:$I$32,'S1'!$B$6:$B$32,$A77,'S1'!$E$6:$E$32,"Ambos")+SUMIFS('S2'!$I$6:$I$23,'S2'!$B$6:$B$23,$A77,'S2'!$E$6:$E$23,"Diego")+SUMIFS('S2'!$I$6:$I$23,'S2'!$B$6:$B$23,$A77,'S2'!$E$6:$E$23,"Ambos")+SUMIFS('S3'!$I$6:$I$24,'S3'!$B$6:$B$24,$A77,'S3'!$E$6:$E$24,"Diego")+SUMIFS('S3'!$I$6:$I$24,'S3'!$B$6:$B$24,$A77,'S3'!$E$6:$E$24,"Ambos")+SUMIFS('S4'!$I$6:$I$22,'S4'!$B$6:$B$22,$A77,'S4'!$E$6:$E$22,"Diego")+SUMIFS('S4'!$I$6:$I$22,'S4'!$B$6:$B$22,$A77,'S4'!$E$6:$E$22,"Ambos")+SUMIFS('S5'!$I$6:$I$20,'S5'!$B$6:$B$20,$A77,'S5'!$E$6:$E$20,"Diego")+SUMIFS('S5'!$I$6:$I$20,'S5'!$B$6:$B$20,$A77,'S5'!$E$6:$E$20,"Ambos")+SUMIFS('S6'!$I$6:$I$17,'S6'!$B$6:$B$17,$A77,'S6'!$E$6:$E$17,"Diego")+SUMIFS('S6'!$I$6:$I$17,'S6'!$B$6:$B$17,$A77,'S6'!$E$6:$E$17,"Ambos")+SUMIFS('S7'!$I$6:$I$19,'S7'!$B$6:$B$19,$A77,'S7'!$E$6:$E$19,"Diego")+SUMIFS('S7'!$I$6:$I$19,'S7'!$B$6:$B$19,$A77,'S7'!$E$6:$E$19,"Ambos")+SUMIFS('S8'!$I$6:$I$23,'S8'!$B$6:$B$23,$A77,'S8'!$E$6:$E$23,"Diego")+SUMIFS('S8'!$I$6:$I$23,'S8'!$B$6:$B$23,$A77,'S8'!$E$6:$E$23,"Ambos")+SUMIFS('S9'!$I$6:$I$15,'S9'!$B$6:$B$15,$A77,'S9'!$E$6:$E$15,"Diego")+SUMIFS('S9'!$I$6:$I$15,'S9'!$B$6:$B$15,$A77,'S9'!$E$6:$E$15,"Ambos")+SUMIFS('S10'!$I$6:$I$13,'S10'!$B$6:$B$13,$A77,'S10'!$E$6:$E$13,"Diego")+SUMIFS('S10'!$I$6:$I$13,'S10'!$B$6:$B$13,$A77,'S10'!$E$6:$E$13,"Ambos")+SUMIFS('Holgura'!$I$6:$I$11,'Holgura'!$B$6:$B$11,$A77,'Holgura'!$E$6:$E$11,"Diego")+SUMIFS('Holgura'!$I$6:$I$11,'Holgura'!$B$6:$B$11,$A77,'Holgura'!$E$6:$E$11,"Ambos")+SUMIFS('Entrega'!$I$6:$I$9,'Entrega'!$B$6:$B$9,$A77,'Entrega'!$E$6:$E$9,"Diego")+SUMIFS('Entrega'!$I$6:$I$9,'Entrega'!$B$6:$B$9,$A77,'Entrega'!$E$6:$E$9,"Ambos")+SUMIFS('Defensa'!$I$6:$I$10,'Defensa'!$B$6:$B$10,$A77,'Defensa'!$E$6:$E$10,"Diego")+SUMIFS('Defensa'!$I$6:$I$10,'Defensa'!$B$6:$B$10,$A77,'Defensa'!$E$6:$E$10,"Ambos")</f>
         <v/>
       </c>
       <c r="F77" s="21">
-        <f>COUNTIFS('S1'!$B$6:$B$32,$A77,'S1'!$E$6:$E$32,"Víctor")+COUNTIFS('S1'!$B$6:$B$32,$A77,'S1'!$E$6:$E$32,"Ambos")+COUNTIFS('S2'!$B$6:$B$23,$A77,'S2'!$E$6:$E$23,"Víctor")+COUNTIFS('S2'!$B$6:$B$23,$A77,'S2'!$E$6:$E$23,"Ambos")+COUNTIFS('S3'!$B$6:$B$19,$A77,'S3'!$E$6:$E$19,"Víctor")+COUNTIFS('S3'!$B$6:$B$19,$A77,'S3'!$E$6:$E$19,"Ambos")+COUNTIFS('S4'!$B$6:$B$20,$A77,'S4'!$E$6:$E$20,"Víctor")+COUNTIFS('S4'!$B$6:$B$20,$A77,'S4'!$E$6:$E$20,"Ambos")+COUNTIFS('S5'!$B$6:$B$20,$A77,'S5'!$E$6:$E$20,"Víctor")+COUNTIFS('S5'!$B$6:$B$20,$A77,'S5'!$E$6:$E$20,"Ambos")+COUNTIFS('S6'!$B$6:$B$17,$A77,'S6'!$E$6:$E$17,"Víctor")+COUNTIFS('S6'!$B$6:$B$17,$A77,'S6'!$E$6:$E$17,"Ambos")+COUNTIFS('S7'!$B$6:$B$19,$A77,'S7'!$E$6:$E$19,"Víctor")+COUNTIFS('S7'!$B$6:$B$19,$A77,'S7'!$E$6:$E$19,"Ambos")+COUNTIFS('S8'!$B$6:$B$23,$A77,'S8'!$E$6:$E$23,"Víctor")+COUNTIFS('S8'!$B$6:$B$23,$A77,'S8'!$E$6:$E$23,"Ambos")+COUNTIFS('S9'!$B$6:$B$15,$A77,'S9'!$E$6:$E$15,"Víctor")+COUNTIFS('S9'!$B$6:$B$15,$A77,'S9'!$E$6:$E$15,"Ambos")+COUNTIFS('S10'!$B$6:$B$13,$A77,'S10'!$E$6:$E$13,"Víctor")+COUNTIFS('S10'!$B$6:$B$13,$A77,'S10'!$E$6:$E$13,"Ambos")+COUNTIFS('Holgura'!$B$6:$B$11,$A77,'Holgura'!$E$6:$E$11,"Víctor")+COUNTIFS('Holgura'!$B$6:$B$11,$A77,'Holgura'!$E$6:$E$11,"Ambos")+COUNTIFS('Entrega'!$B$6:$B$9,$A77,'Entrega'!$E$6:$E$9,"Víctor")+COUNTIFS('Entrega'!$B$6:$B$9,$A77,'Entrega'!$E$6:$E$9,"Ambos")+COUNTIFS('Defensa'!$B$6:$B$10,$A77,'Defensa'!$E$6:$E$10,"Víctor")+COUNTIFS('Defensa'!$B$6:$B$10,$A77,'Defensa'!$E$6:$E$10,"Ambos")</f>
+        <f>COUNTIFS('S1'!$B$6:$B$32,$A77,'S1'!$E$6:$E$32,"Víctor")+COUNTIFS('S1'!$B$6:$B$32,$A77,'S1'!$E$6:$E$32,"Ambos")+COUNTIFS('S2'!$B$6:$B$23,$A77,'S2'!$E$6:$E$23,"Víctor")+COUNTIFS('S2'!$B$6:$B$23,$A77,'S2'!$E$6:$E$23,"Ambos")+COUNTIFS('S3'!$B$6:$B$24,$A77,'S3'!$E$6:$E$24,"Víctor")+COUNTIFS('S3'!$B$6:$B$24,$A77,'S3'!$E$6:$E$24,"Ambos")+COUNTIFS('S4'!$B$6:$B$22,$A77,'S4'!$E$6:$E$22,"Víctor")+COUNTIFS('S4'!$B$6:$B$22,$A77,'S4'!$E$6:$E$22,"Ambos")+COUNTIFS('S5'!$B$6:$B$20,$A77,'S5'!$E$6:$E$20,"Víctor")+COUNTIFS('S5'!$B$6:$B$20,$A77,'S5'!$E$6:$E$20,"Ambos")+COUNTIFS('S6'!$B$6:$B$17,$A77,'S6'!$E$6:$E$17,"Víctor")+COUNTIFS('S6'!$B$6:$B$17,$A77,'S6'!$E$6:$E$17,"Ambos")+COUNTIFS('S7'!$B$6:$B$19,$A77,'S7'!$E$6:$E$19,"Víctor")+COUNTIFS('S7'!$B$6:$B$19,$A77,'S7'!$E$6:$E$19,"Ambos")+COUNTIFS('S8'!$B$6:$B$23,$A77,'S8'!$E$6:$E$23,"Víctor")+COUNTIFS('S8'!$B$6:$B$23,$A77,'S8'!$E$6:$E$23,"Ambos")+COUNTIFS('S9'!$B$6:$B$15,$A77,'S9'!$E$6:$E$15,"Víctor")+COUNTIFS('S9'!$B$6:$B$15,$A77,'S9'!$E$6:$E$15,"Ambos")+COUNTIFS('S10'!$B$6:$B$13,$A77,'S10'!$E$6:$E$13,"Víctor")+COUNTIFS('S10'!$B$6:$B$13,$A77,'S10'!$E$6:$E$13,"Ambos")+COUNTIFS('Holgura'!$B$6:$B$11,$A77,'Holgura'!$E$6:$E$11,"Víctor")+COUNTIFS('Holgura'!$B$6:$B$11,$A77,'Holgura'!$E$6:$E$11,"Ambos")+COUNTIFS('Entrega'!$B$6:$B$9,$A77,'Entrega'!$E$6:$E$9,"Víctor")+COUNTIFS('Entrega'!$B$6:$B$9,$A77,'Entrega'!$E$6:$E$9,"Ambos")+COUNTIFS('Defensa'!$B$6:$B$10,$A77,'Defensa'!$E$6:$E$10,"Víctor")+COUNTIFS('Defensa'!$B$6:$B$10,$A77,'Defensa'!$E$6:$E$10,"Ambos")</f>
         <v/>
       </c>
       <c r="G77" s="21">
-        <f>COUNTIFS('S1'!$B$6:$B$32,$A77,'S1'!$E$6:$E$32,"Diego")+COUNTIFS('S1'!$B$6:$B$32,$A77,'S1'!$E$6:$E$32,"Ambos")+COUNTIFS('S2'!$B$6:$B$23,$A77,'S2'!$E$6:$E$23,"Diego")+COUNTIFS('S2'!$B$6:$B$23,$A77,'S2'!$E$6:$E$23,"Ambos")+COUNTIFS('S3'!$B$6:$B$19,$A77,'S3'!$E$6:$E$19,"Diego")+COUNTIFS('S3'!$B$6:$B$19,$A77,'S3'!$E$6:$E$19,"Ambos")+COUNTIFS('S4'!$B$6:$B$20,$A77,'S4'!$E$6:$E$20,"Diego")+COUNTIFS('S4'!$B$6:$B$20,$A77,'S4'!$E$6:$E$20,"Ambos")+COUNTIFS('S5'!$B$6:$B$20,$A77,'S5'!$E$6:$E$20,"Diego")+COUNTIFS('S5'!$B$6:$B$20,$A77,'S5'!$E$6:$E$20,"Ambos")+COUNTIFS('S6'!$B$6:$B$17,$A77,'S6'!$E$6:$E$17,"Diego")+COUNTIFS('S6'!$B$6:$B$17,$A77,'S6'!$E$6:$E$17,"Ambos")+COUNTIFS('S7'!$B$6:$B$19,$A77,'S7'!$E$6:$E$19,"Diego")+COUNTIFS('S7'!$B$6:$B$19,$A77,'S7'!$E$6:$E$19,"Ambos")+COUNTIFS('S8'!$B$6:$B$23,$A77,'S8'!$E$6:$E$23,"Diego")+COUNTIFS('S8'!$B$6:$B$23,$A77,'S8'!$E$6:$E$23,"Ambos")+COUNTIFS('S9'!$B$6:$B$15,$A77,'S9'!$E$6:$E$15,"Diego")+COUNTIFS('S9'!$B$6:$B$15,$A77,'S9'!$E$6:$E$15,"Ambos")+COUNTIFS('S10'!$B$6:$B$13,$A77,'S10'!$E$6:$E$13,"Diego")+COUNTIFS('S10'!$B$6:$B$13,$A77,'S10'!$E$6:$E$13,"Ambos")+COUNTIFS('Holgura'!$B$6:$B$11,$A77,'Holgura'!$E$6:$E$11,"Diego")+COUNTIFS('Holgura'!$B$6:$B$11,$A77,'Holgura'!$E$6:$E$11,"Ambos")+COUNTIFS('Entrega'!$B$6:$B$9,$A77,'Entrega'!$E$6:$E$9,"Diego")+COUNTIFS('Entrega'!$B$6:$B$9,$A77,'Entrega'!$E$6:$E$9,"Ambos")+COUNTIFS('Defensa'!$B$6:$B$10,$A77,'Defensa'!$E$6:$E$10,"Diego")+COUNTIFS('Defensa'!$B$6:$B$10,$A77,'Defensa'!$E$6:$E$10,"Ambos")</f>
+        <f>COUNTIFS('S1'!$B$6:$B$32,$A77,'S1'!$E$6:$E$32,"Diego")+COUNTIFS('S1'!$B$6:$B$32,$A77,'S1'!$E$6:$E$32,"Ambos")+COUNTIFS('S2'!$B$6:$B$23,$A77,'S2'!$E$6:$E$23,"Diego")+COUNTIFS('S2'!$B$6:$B$23,$A77,'S2'!$E$6:$E$23,"Ambos")+COUNTIFS('S3'!$B$6:$B$24,$A77,'S3'!$E$6:$E$24,"Diego")+COUNTIFS('S3'!$B$6:$B$24,$A77,'S3'!$E$6:$E$24,"Ambos")+COUNTIFS('S4'!$B$6:$B$22,$A77,'S4'!$E$6:$E$22,"Diego")+COUNTIFS('S4'!$B$6:$B$22,$A77,'S4'!$E$6:$E$22,"Ambos")+COUNTIFS('S5'!$B$6:$B$20,$A77,'S5'!$E$6:$E$20,"Diego")+COUNTIFS('S5'!$B$6:$B$20,$A77,'S5'!$E$6:$E$20,"Ambos")+COUNTIFS('S6'!$B$6:$B$17,$A77,'S6'!$E$6:$E$17,"Diego")+COUNTIFS('S6'!$B$6:$B$17,$A77,'S6'!$E$6:$E$17,"Ambos")+COUNTIFS('S7'!$B$6:$B$19,$A77,'S7'!$E$6:$E$19,"Diego")+COUNTIFS('S7'!$B$6:$B$19,$A77,'S7'!$E$6:$E$19,"Ambos")+COUNTIFS('S8'!$B$6:$B$23,$A77,'S8'!$E$6:$E$23,"Diego")+COUNTIFS('S8'!$B$6:$B$23,$A77,'S8'!$E$6:$E$23,"Ambos")+COUNTIFS('S9'!$B$6:$B$15,$A77,'S9'!$E$6:$E$15,"Diego")+COUNTIFS('S9'!$B$6:$B$15,$A77,'S9'!$E$6:$E$15,"Ambos")+COUNTIFS('S10'!$B$6:$B$13,$A77,'S10'!$E$6:$E$13,"Diego")+COUNTIFS('S10'!$B$6:$B$13,$A77,'S10'!$E$6:$E$13,"Ambos")+COUNTIFS('Holgura'!$B$6:$B$11,$A77,'Holgura'!$E$6:$E$11,"Diego")+COUNTIFS('Holgura'!$B$6:$B$11,$A77,'Holgura'!$E$6:$E$11,"Ambos")+COUNTIFS('Entrega'!$B$6:$B$9,$A77,'Entrega'!$E$6:$E$9,"Diego")+COUNTIFS('Entrega'!$B$6:$B$9,$A77,'Entrega'!$E$6:$E$9,"Ambos")+COUNTIFS('Defensa'!$B$6:$B$10,$A77,'Defensa'!$E$6:$E$10,"Diego")+COUNTIFS('Defensa'!$B$6:$B$10,$A77,'Defensa'!$E$6:$E$10,"Ambos")</f>
         <v/>
       </c>
     </row>
@@ -10797,19 +10818,19 @@
         <v/>
       </c>
       <c r="D78" s="21">
-        <f>SUMIFS('S1'!$I$6:$I$32,'S1'!$B$6:$B$32,$A78,'S1'!$E$6:$E$32,"Víctor")+SUMIFS('S1'!$I$6:$I$32,'S1'!$B$6:$B$32,$A78,'S1'!$E$6:$E$32,"Ambos")+SUMIFS('S2'!$I$6:$I$23,'S2'!$B$6:$B$23,$A78,'S2'!$E$6:$E$23,"Víctor")+SUMIFS('S2'!$I$6:$I$23,'S2'!$B$6:$B$23,$A78,'S2'!$E$6:$E$23,"Ambos")+SUMIFS('S3'!$I$6:$I$19,'S3'!$B$6:$B$19,$A78,'S3'!$E$6:$E$19,"Víctor")+SUMIFS('S3'!$I$6:$I$19,'S3'!$B$6:$B$19,$A78,'S3'!$E$6:$E$19,"Ambos")+SUMIFS('S4'!$I$6:$I$20,'S4'!$B$6:$B$20,$A78,'S4'!$E$6:$E$20,"Víctor")+SUMIFS('S4'!$I$6:$I$20,'S4'!$B$6:$B$20,$A78,'S4'!$E$6:$E$20,"Ambos")+SUMIFS('S5'!$I$6:$I$20,'S5'!$B$6:$B$20,$A78,'S5'!$E$6:$E$20,"Víctor")+SUMIFS('S5'!$I$6:$I$20,'S5'!$B$6:$B$20,$A78,'S5'!$E$6:$E$20,"Ambos")+SUMIFS('S6'!$I$6:$I$17,'S6'!$B$6:$B$17,$A78,'S6'!$E$6:$E$17,"Víctor")+SUMIFS('S6'!$I$6:$I$17,'S6'!$B$6:$B$17,$A78,'S6'!$E$6:$E$17,"Ambos")+SUMIFS('S7'!$I$6:$I$19,'S7'!$B$6:$B$19,$A78,'S7'!$E$6:$E$19,"Víctor")+SUMIFS('S7'!$I$6:$I$19,'S7'!$B$6:$B$19,$A78,'S7'!$E$6:$E$19,"Ambos")+SUMIFS('S8'!$I$6:$I$23,'S8'!$B$6:$B$23,$A78,'S8'!$E$6:$E$23,"Víctor")+SUMIFS('S8'!$I$6:$I$23,'S8'!$B$6:$B$23,$A78,'S8'!$E$6:$E$23,"Ambos")+SUMIFS('S9'!$I$6:$I$15,'S9'!$B$6:$B$15,$A78,'S9'!$E$6:$E$15,"Víctor")+SUMIFS('S9'!$I$6:$I$15,'S9'!$B$6:$B$15,$A78,'S9'!$E$6:$E$15,"Ambos")+SUMIFS('S10'!$I$6:$I$13,'S10'!$B$6:$B$13,$A78,'S10'!$E$6:$E$13,"Víctor")+SUMIFS('S10'!$I$6:$I$13,'S10'!$B$6:$B$13,$A78,'S10'!$E$6:$E$13,"Ambos")+SUMIFS('Holgura'!$I$6:$I$11,'Holgura'!$B$6:$B$11,$A78,'Holgura'!$E$6:$E$11,"Víctor")+SUMIFS('Holgura'!$I$6:$I$11,'Holgura'!$B$6:$B$11,$A78,'Holgura'!$E$6:$E$11,"Ambos")+SUMIFS('Entrega'!$I$6:$I$9,'Entrega'!$B$6:$B$9,$A78,'Entrega'!$E$6:$E$9,"Víctor")+SUMIFS('Entrega'!$I$6:$I$9,'Entrega'!$B$6:$B$9,$A78,'Entrega'!$E$6:$E$9,"Ambos")+SUMIFS('Defensa'!$I$6:$I$10,'Defensa'!$B$6:$B$10,$A78,'Defensa'!$E$6:$E$10,"Víctor")+SUMIFS('Defensa'!$I$6:$I$10,'Defensa'!$B$6:$B$10,$A78,'Defensa'!$E$6:$E$10,"Ambos")</f>
+        <f>SUMIFS('S1'!$I$6:$I$32,'S1'!$B$6:$B$32,$A78,'S1'!$E$6:$E$32,"Víctor")+SUMIFS('S1'!$I$6:$I$32,'S1'!$B$6:$B$32,$A78,'S1'!$E$6:$E$32,"Ambos")+SUMIFS('S2'!$I$6:$I$23,'S2'!$B$6:$B$23,$A78,'S2'!$E$6:$E$23,"Víctor")+SUMIFS('S2'!$I$6:$I$23,'S2'!$B$6:$B$23,$A78,'S2'!$E$6:$E$23,"Ambos")+SUMIFS('S3'!$I$6:$I$24,'S3'!$B$6:$B$24,$A78,'S3'!$E$6:$E$24,"Víctor")+SUMIFS('S3'!$I$6:$I$24,'S3'!$B$6:$B$24,$A78,'S3'!$E$6:$E$24,"Ambos")+SUMIFS('S4'!$I$6:$I$22,'S4'!$B$6:$B$22,$A78,'S4'!$E$6:$E$22,"Víctor")+SUMIFS('S4'!$I$6:$I$22,'S4'!$B$6:$B$22,$A78,'S4'!$E$6:$E$22,"Ambos")+SUMIFS('S5'!$I$6:$I$20,'S5'!$B$6:$B$20,$A78,'S5'!$E$6:$E$20,"Víctor")+SUMIFS('S5'!$I$6:$I$20,'S5'!$B$6:$B$20,$A78,'S5'!$E$6:$E$20,"Ambos")+SUMIFS('S6'!$I$6:$I$17,'S6'!$B$6:$B$17,$A78,'S6'!$E$6:$E$17,"Víctor")+SUMIFS('S6'!$I$6:$I$17,'S6'!$B$6:$B$17,$A78,'S6'!$E$6:$E$17,"Ambos")+SUMIFS('S7'!$I$6:$I$19,'S7'!$B$6:$B$19,$A78,'S7'!$E$6:$E$19,"Víctor")+SUMIFS('S7'!$I$6:$I$19,'S7'!$B$6:$B$19,$A78,'S7'!$E$6:$E$19,"Ambos")+SUMIFS('S8'!$I$6:$I$23,'S8'!$B$6:$B$23,$A78,'S8'!$E$6:$E$23,"Víctor")+SUMIFS('S8'!$I$6:$I$23,'S8'!$B$6:$B$23,$A78,'S8'!$E$6:$E$23,"Ambos")+SUMIFS('S9'!$I$6:$I$15,'S9'!$B$6:$B$15,$A78,'S9'!$E$6:$E$15,"Víctor")+SUMIFS('S9'!$I$6:$I$15,'S9'!$B$6:$B$15,$A78,'S9'!$E$6:$E$15,"Ambos")+SUMIFS('S10'!$I$6:$I$13,'S10'!$B$6:$B$13,$A78,'S10'!$E$6:$E$13,"Víctor")+SUMIFS('S10'!$I$6:$I$13,'S10'!$B$6:$B$13,$A78,'S10'!$E$6:$E$13,"Ambos")+SUMIFS('Holgura'!$I$6:$I$11,'Holgura'!$B$6:$B$11,$A78,'Holgura'!$E$6:$E$11,"Víctor")+SUMIFS('Holgura'!$I$6:$I$11,'Holgura'!$B$6:$B$11,$A78,'Holgura'!$E$6:$E$11,"Ambos")+SUMIFS('Entrega'!$I$6:$I$9,'Entrega'!$B$6:$B$9,$A78,'Entrega'!$E$6:$E$9,"Víctor")+SUMIFS('Entrega'!$I$6:$I$9,'Entrega'!$B$6:$B$9,$A78,'Entrega'!$E$6:$E$9,"Ambos")+SUMIFS('Defensa'!$I$6:$I$10,'Defensa'!$B$6:$B$10,$A78,'Defensa'!$E$6:$E$10,"Víctor")+SUMIFS('Defensa'!$I$6:$I$10,'Defensa'!$B$6:$B$10,$A78,'Defensa'!$E$6:$E$10,"Ambos")</f>
         <v/>
       </c>
       <c r="E78" s="21">
-        <f>SUMIFS('S1'!$I$6:$I$32,'S1'!$B$6:$B$32,$A78,'S1'!$E$6:$E$32,"Diego")+SUMIFS('S1'!$I$6:$I$32,'S1'!$B$6:$B$32,$A78,'S1'!$E$6:$E$32,"Ambos")+SUMIFS('S2'!$I$6:$I$23,'S2'!$B$6:$B$23,$A78,'S2'!$E$6:$E$23,"Diego")+SUMIFS('S2'!$I$6:$I$23,'S2'!$B$6:$B$23,$A78,'S2'!$E$6:$E$23,"Ambos")+SUMIFS('S3'!$I$6:$I$19,'S3'!$B$6:$B$19,$A78,'S3'!$E$6:$E$19,"Diego")+SUMIFS('S3'!$I$6:$I$19,'S3'!$B$6:$B$19,$A78,'S3'!$E$6:$E$19,"Ambos")+SUMIFS('S4'!$I$6:$I$20,'S4'!$B$6:$B$20,$A78,'S4'!$E$6:$E$20,"Diego")+SUMIFS('S4'!$I$6:$I$20,'S4'!$B$6:$B$20,$A78,'S4'!$E$6:$E$20,"Ambos")+SUMIFS('S5'!$I$6:$I$20,'S5'!$B$6:$B$20,$A78,'S5'!$E$6:$E$20,"Diego")+SUMIFS('S5'!$I$6:$I$20,'S5'!$B$6:$B$20,$A78,'S5'!$E$6:$E$20,"Ambos")+SUMIFS('S6'!$I$6:$I$17,'S6'!$B$6:$B$17,$A78,'S6'!$E$6:$E$17,"Diego")+SUMIFS('S6'!$I$6:$I$17,'S6'!$B$6:$B$17,$A78,'S6'!$E$6:$E$17,"Ambos")+SUMIFS('S7'!$I$6:$I$19,'S7'!$B$6:$B$19,$A78,'S7'!$E$6:$E$19,"Diego")+SUMIFS('S7'!$I$6:$I$19,'S7'!$B$6:$B$19,$A78,'S7'!$E$6:$E$19,"Ambos")+SUMIFS('S8'!$I$6:$I$23,'S8'!$B$6:$B$23,$A78,'S8'!$E$6:$E$23,"Diego")+SUMIFS('S8'!$I$6:$I$23,'S8'!$B$6:$B$23,$A78,'S8'!$E$6:$E$23,"Ambos")+SUMIFS('S9'!$I$6:$I$15,'S9'!$B$6:$B$15,$A78,'S9'!$E$6:$E$15,"Diego")+SUMIFS('S9'!$I$6:$I$15,'S9'!$B$6:$B$15,$A78,'S9'!$E$6:$E$15,"Ambos")+SUMIFS('S10'!$I$6:$I$13,'S10'!$B$6:$B$13,$A78,'S10'!$E$6:$E$13,"Diego")+SUMIFS('S10'!$I$6:$I$13,'S10'!$B$6:$B$13,$A78,'S10'!$E$6:$E$13,"Ambos")+SUMIFS('Holgura'!$I$6:$I$11,'Holgura'!$B$6:$B$11,$A78,'Holgura'!$E$6:$E$11,"Diego")+SUMIFS('Holgura'!$I$6:$I$11,'Holgura'!$B$6:$B$11,$A78,'Holgura'!$E$6:$E$11,"Ambos")+SUMIFS('Entrega'!$I$6:$I$9,'Entrega'!$B$6:$B$9,$A78,'Entrega'!$E$6:$E$9,"Diego")+SUMIFS('Entrega'!$I$6:$I$9,'Entrega'!$B$6:$B$9,$A78,'Entrega'!$E$6:$E$9,"Ambos")+SUMIFS('Defensa'!$I$6:$I$10,'Defensa'!$B$6:$B$10,$A78,'Defensa'!$E$6:$E$10,"Diego")+SUMIFS('Defensa'!$I$6:$I$10,'Defensa'!$B$6:$B$10,$A78,'Defensa'!$E$6:$E$10,"Ambos")</f>
+        <f>SUMIFS('S1'!$I$6:$I$32,'S1'!$B$6:$B$32,$A78,'S1'!$E$6:$E$32,"Diego")+SUMIFS('S1'!$I$6:$I$32,'S1'!$B$6:$B$32,$A78,'S1'!$E$6:$E$32,"Ambos")+SUMIFS('S2'!$I$6:$I$23,'S2'!$B$6:$B$23,$A78,'S2'!$E$6:$E$23,"Diego")+SUMIFS('S2'!$I$6:$I$23,'S2'!$B$6:$B$23,$A78,'S2'!$E$6:$E$23,"Ambos")+SUMIFS('S3'!$I$6:$I$24,'S3'!$B$6:$B$24,$A78,'S3'!$E$6:$E$24,"Diego")+SUMIFS('S3'!$I$6:$I$24,'S3'!$B$6:$B$24,$A78,'S3'!$E$6:$E$24,"Ambos")+SUMIFS('S4'!$I$6:$I$22,'S4'!$B$6:$B$22,$A78,'S4'!$E$6:$E$22,"Diego")+SUMIFS('S4'!$I$6:$I$22,'S4'!$B$6:$B$22,$A78,'S4'!$E$6:$E$22,"Ambos")+SUMIFS('S5'!$I$6:$I$20,'S5'!$B$6:$B$20,$A78,'S5'!$E$6:$E$20,"Diego")+SUMIFS('S5'!$I$6:$I$20,'S5'!$B$6:$B$20,$A78,'S5'!$E$6:$E$20,"Ambos")+SUMIFS('S6'!$I$6:$I$17,'S6'!$B$6:$B$17,$A78,'S6'!$E$6:$E$17,"Diego")+SUMIFS('S6'!$I$6:$I$17,'S6'!$B$6:$B$17,$A78,'S6'!$E$6:$E$17,"Ambos")+SUMIFS('S7'!$I$6:$I$19,'S7'!$B$6:$B$19,$A78,'S7'!$E$6:$E$19,"Diego")+SUMIFS('S7'!$I$6:$I$19,'S7'!$B$6:$B$19,$A78,'S7'!$E$6:$E$19,"Ambos")+SUMIFS('S8'!$I$6:$I$23,'S8'!$B$6:$B$23,$A78,'S8'!$E$6:$E$23,"Diego")+SUMIFS('S8'!$I$6:$I$23,'S8'!$B$6:$B$23,$A78,'S8'!$E$6:$E$23,"Ambos")+SUMIFS('S9'!$I$6:$I$15,'S9'!$B$6:$B$15,$A78,'S9'!$E$6:$E$15,"Diego")+SUMIFS('S9'!$I$6:$I$15,'S9'!$B$6:$B$15,$A78,'S9'!$E$6:$E$15,"Ambos")+SUMIFS('S10'!$I$6:$I$13,'S10'!$B$6:$B$13,$A78,'S10'!$E$6:$E$13,"Diego")+SUMIFS('S10'!$I$6:$I$13,'S10'!$B$6:$B$13,$A78,'S10'!$E$6:$E$13,"Ambos")+SUMIFS('Holgura'!$I$6:$I$11,'Holgura'!$B$6:$B$11,$A78,'Holgura'!$E$6:$E$11,"Diego")+SUMIFS('Holgura'!$I$6:$I$11,'Holgura'!$B$6:$B$11,$A78,'Holgura'!$E$6:$E$11,"Ambos")+SUMIFS('Entrega'!$I$6:$I$9,'Entrega'!$B$6:$B$9,$A78,'Entrega'!$E$6:$E$9,"Diego")+SUMIFS('Entrega'!$I$6:$I$9,'Entrega'!$B$6:$B$9,$A78,'Entrega'!$E$6:$E$9,"Ambos")+SUMIFS('Defensa'!$I$6:$I$10,'Defensa'!$B$6:$B$10,$A78,'Defensa'!$E$6:$E$10,"Diego")+SUMIFS('Defensa'!$I$6:$I$10,'Defensa'!$B$6:$B$10,$A78,'Defensa'!$E$6:$E$10,"Ambos")</f>
         <v/>
       </c>
       <c r="F78" s="21">
-        <f>COUNTIFS('S1'!$B$6:$B$32,$A78,'S1'!$E$6:$E$32,"Víctor")+COUNTIFS('S1'!$B$6:$B$32,$A78,'S1'!$E$6:$E$32,"Ambos")+COUNTIFS('S2'!$B$6:$B$23,$A78,'S2'!$E$6:$E$23,"Víctor")+COUNTIFS('S2'!$B$6:$B$23,$A78,'S2'!$E$6:$E$23,"Ambos")+COUNTIFS('S3'!$B$6:$B$19,$A78,'S3'!$E$6:$E$19,"Víctor")+COUNTIFS('S3'!$B$6:$B$19,$A78,'S3'!$E$6:$E$19,"Ambos")+COUNTIFS('S4'!$B$6:$B$20,$A78,'S4'!$E$6:$E$20,"Víctor")+COUNTIFS('S4'!$B$6:$B$20,$A78,'S4'!$E$6:$E$20,"Ambos")+COUNTIFS('S5'!$B$6:$B$20,$A78,'S5'!$E$6:$E$20,"Víctor")+COUNTIFS('S5'!$B$6:$B$20,$A78,'S5'!$E$6:$E$20,"Ambos")+COUNTIFS('S6'!$B$6:$B$17,$A78,'S6'!$E$6:$E$17,"Víctor")+COUNTIFS('S6'!$B$6:$B$17,$A78,'S6'!$E$6:$E$17,"Ambos")+COUNTIFS('S7'!$B$6:$B$19,$A78,'S7'!$E$6:$E$19,"Víctor")+COUNTIFS('S7'!$B$6:$B$19,$A78,'S7'!$E$6:$E$19,"Ambos")+COUNTIFS('S8'!$B$6:$B$23,$A78,'S8'!$E$6:$E$23,"Víctor")+COUNTIFS('S8'!$B$6:$B$23,$A78,'S8'!$E$6:$E$23,"Ambos")+COUNTIFS('S9'!$B$6:$B$15,$A78,'S9'!$E$6:$E$15,"Víctor")+COUNTIFS('S9'!$B$6:$B$15,$A78,'S9'!$E$6:$E$15,"Ambos")+COUNTIFS('S10'!$B$6:$B$13,$A78,'S10'!$E$6:$E$13,"Víctor")+COUNTIFS('S10'!$B$6:$B$13,$A78,'S10'!$E$6:$E$13,"Ambos")+COUNTIFS('Holgura'!$B$6:$B$11,$A78,'Holgura'!$E$6:$E$11,"Víctor")+COUNTIFS('Holgura'!$B$6:$B$11,$A78,'Holgura'!$E$6:$E$11,"Ambos")+COUNTIFS('Entrega'!$B$6:$B$9,$A78,'Entrega'!$E$6:$E$9,"Víctor")+COUNTIFS('Entrega'!$B$6:$B$9,$A78,'Entrega'!$E$6:$E$9,"Ambos")+COUNTIFS('Defensa'!$B$6:$B$10,$A78,'Defensa'!$E$6:$E$10,"Víctor")+COUNTIFS('Defensa'!$B$6:$B$10,$A78,'Defensa'!$E$6:$E$10,"Ambos")</f>
+        <f>COUNTIFS('S1'!$B$6:$B$32,$A78,'S1'!$E$6:$E$32,"Víctor")+COUNTIFS('S1'!$B$6:$B$32,$A78,'S1'!$E$6:$E$32,"Ambos")+COUNTIFS('S2'!$B$6:$B$23,$A78,'S2'!$E$6:$E$23,"Víctor")+COUNTIFS('S2'!$B$6:$B$23,$A78,'S2'!$E$6:$E$23,"Ambos")+COUNTIFS('S3'!$B$6:$B$24,$A78,'S3'!$E$6:$E$24,"Víctor")+COUNTIFS('S3'!$B$6:$B$24,$A78,'S3'!$E$6:$E$24,"Ambos")+COUNTIFS('S4'!$B$6:$B$22,$A78,'S4'!$E$6:$E$22,"Víctor")+COUNTIFS('S4'!$B$6:$B$22,$A78,'S4'!$E$6:$E$22,"Ambos")+COUNTIFS('S5'!$B$6:$B$20,$A78,'S5'!$E$6:$E$20,"Víctor")+COUNTIFS('S5'!$B$6:$B$20,$A78,'S5'!$E$6:$E$20,"Ambos")+COUNTIFS('S6'!$B$6:$B$17,$A78,'S6'!$E$6:$E$17,"Víctor")+COUNTIFS('S6'!$B$6:$B$17,$A78,'S6'!$E$6:$E$17,"Ambos")+COUNTIFS('S7'!$B$6:$B$19,$A78,'S7'!$E$6:$E$19,"Víctor")+COUNTIFS('S7'!$B$6:$B$19,$A78,'S7'!$E$6:$E$19,"Ambos")+COUNTIFS('S8'!$B$6:$B$23,$A78,'S8'!$E$6:$E$23,"Víctor")+COUNTIFS('S8'!$B$6:$B$23,$A78,'S8'!$E$6:$E$23,"Ambos")+COUNTIFS('S9'!$B$6:$B$15,$A78,'S9'!$E$6:$E$15,"Víctor")+COUNTIFS('S9'!$B$6:$B$15,$A78,'S9'!$E$6:$E$15,"Ambos")+COUNTIFS('S10'!$B$6:$B$13,$A78,'S10'!$E$6:$E$13,"Víctor")+COUNTIFS('S10'!$B$6:$B$13,$A78,'S10'!$E$6:$E$13,"Ambos")+COUNTIFS('Holgura'!$B$6:$B$11,$A78,'Holgura'!$E$6:$E$11,"Víctor")+COUNTIFS('Holgura'!$B$6:$B$11,$A78,'Holgura'!$E$6:$E$11,"Ambos")+COUNTIFS('Entrega'!$B$6:$B$9,$A78,'Entrega'!$E$6:$E$9,"Víctor")+COUNTIFS('Entrega'!$B$6:$B$9,$A78,'Entrega'!$E$6:$E$9,"Ambos")+COUNTIFS('Defensa'!$B$6:$B$10,$A78,'Defensa'!$E$6:$E$10,"Víctor")+COUNTIFS('Defensa'!$B$6:$B$10,$A78,'Defensa'!$E$6:$E$10,"Ambos")</f>
         <v/>
       </c>
       <c r="G78" s="21">
-        <f>COUNTIFS('S1'!$B$6:$B$32,$A78,'S1'!$E$6:$E$32,"Diego")+COUNTIFS('S1'!$B$6:$B$32,$A78,'S1'!$E$6:$E$32,"Ambos")+COUNTIFS('S2'!$B$6:$B$23,$A78,'S2'!$E$6:$E$23,"Diego")+COUNTIFS('S2'!$B$6:$B$23,$A78,'S2'!$E$6:$E$23,"Ambos")+COUNTIFS('S3'!$B$6:$B$19,$A78,'S3'!$E$6:$E$19,"Diego")+COUNTIFS('S3'!$B$6:$B$19,$A78,'S3'!$E$6:$E$19,"Ambos")+COUNTIFS('S4'!$B$6:$B$20,$A78,'S4'!$E$6:$E$20,"Diego")+COUNTIFS('S4'!$B$6:$B$20,$A78,'S4'!$E$6:$E$20,"Ambos")+COUNTIFS('S5'!$B$6:$B$20,$A78,'S5'!$E$6:$E$20,"Diego")+COUNTIFS('S5'!$B$6:$B$20,$A78,'S5'!$E$6:$E$20,"Ambos")+COUNTIFS('S6'!$B$6:$B$17,$A78,'S6'!$E$6:$E$17,"Diego")+COUNTIFS('S6'!$B$6:$B$17,$A78,'S6'!$E$6:$E$17,"Ambos")+COUNTIFS('S7'!$B$6:$B$19,$A78,'S7'!$E$6:$E$19,"Diego")+COUNTIFS('S7'!$B$6:$B$19,$A78,'S7'!$E$6:$E$19,"Ambos")+COUNTIFS('S8'!$B$6:$B$23,$A78,'S8'!$E$6:$E$23,"Diego")+COUNTIFS('S8'!$B$6:$B$23,$A78,'S8'!$E$6:$E$23,"Ambos")+COUNTIFS('S9'!$B$6:$B$15,$A78,'S9'!$E$6:$E$15,"Diego")+COUNTIFS('S9'!$B$6:$B$15,$A78,'S9'!$E$6:$E$15,"Ambos")+COUNTIFS('S10'!$B$6:$B$13,$A78,'S10'!$E$6:$E$13,"Diego")+COUNTIFS('S10'!$B$6:$B$13,$A78,'S10'!$E$6:$E$13,"Ambos")+COUNTIFS('Holgura'!$B$6:$B$11,$A78,'Holgura'!$E$6:$E$11,"Diego")+COUNTIFS('Holgura'!$B$6:$B$11,$A78,'Holgura'!$E$6:$E$11,"Ambos")+COUNTIFS('Entrega'!$B$6:$B$9,$A78,'Entrega'!$E$6:$E$9,"Diego")+COUNTIFS('Entrega'!$B$6:$B$9,$A78,'Entrega'!$E$6:$E$9,"Ambos")+COUNTIFS('Defensa'!$B$6:$B$10,$A78,'Defensa'!$E$6:$E$10,"Diego")+COUNTIFS('Defensa'!$B$6:$B$10,$A78,'Defensa'!$E$6:$E$10,"Ambos")</f>
+        <f>COUNTIFS('S1'!$B$6:$B$32,$A78,'S1'!$E$6:$E$32,"Diego")+COUNTIFS('S1'!$B$6:$B$32,$A78,'S1'!$E$6:$E$32,"Ambos")+COUNTIFS('S2'!$B$6:$B$23,$A78,'S2'!$E$6:$E$23,"Diego")+COUNTIFS('S2'!$B$6:$B$23,$A78,'S2'!$E$6:$E$23,"Ambos")+COUNTIFS('S3'!$B$6:$B$24,$A78,'S3'!$E$6:$E$24,"Diego")+COUNTIFS('S3'!$B$6:$B$24,$A78,'S3'!$E$6:$E$24,"Ambos")+COUNTIFS('S4'!$B$6:$B$22,$A78,'S4'!$E$6:$E$22,"Diego")+COUNTIFS('S4'!$B$6:$B$22,$A78,'S4'!$E$6:$E$22,"Ambos")+COUNTIFS('S5'!$B$6:$B$20,$A78,'S5'!$E$6:$E$20,"Diego")+COUNTIFS('S5'!$B$6:$B$20,$A78,'S5'!$E$6:$E$20,"Ambos")+COUNTIFS('S6'!$B$6:$B$17,$A78,'S6'!$E$6:$E$17,"Diego")+COUNTIFS('S6'!$B$6:$B$17,$A78,'S6'!$E$6:$E$17,"Ambos")+COUNTIFS('S7'!$B$6:$B$19,$A78,'S7'!$E$6:$E$19,"Diego")+COUNTIFS('S7'!$B$6:$B$19,$A78,'S7'!$E$6:$E$19,"Ambos")+COUNTIFS('S8'!$B$6:$B$23,$A78,'S8'!$E$6:$E$23,"Diego")+COUNTIFS('S8'!$B$6:$B$23,$A78,'S8'!$E$6:$E$23,"Ambos")+COUNTIFS('S9'!$B$6:$B$15,$A78,'S9'!$E$6:$E$15,"Diego")+COUNTIFS('S9'!$B$6:$B$15,$A78,'S9'!$E$6:$E$15,"Ambos")+COUNTIFS('S10'!$B$6:$B$13,$A78,'S10'!$E$6:$E$13,"Diego")+COUNTIFS('S10'!$B$6:$B$13,$A78,'S10'!$E$6:$E$13,"Ambos")+COUNTIFS('Holgura'!$B$6:$B$11,$A78,'Holgura'!$E$6:$E$11,"Diego")+COUNTIFS('Holgura'!$B$6:$B$11,$A78,'Holgura'!$E$6:$E$11,"Ambos")+COUNTIFS('Entrega'!$B$6:$B$9,$A78,'Entrega'!$E$6:$E$9,"Diego")+COUNTIFS('Entrega'!$B$6:$B$9,$A78,'Entrega'!$E$6:$E$9,"Ambos")+COUNTIFS('Defensa'!$B$6:$B$10,$A78,'Defensa'!$E$6:$E$10,"Diego")+COUNTIFS('Defensa'!$B$6:$B$10,$A78,'Defensa'!$E$6:$E$10,"Ambos")</f>
         <v/>
       </c>
     </row>
@@ -10826,19 +10847,19 @@
         <v/>
       </c>
       <c r="D79" s="21">
-        <f>SUMIFS('S1'!$I$6:$I$32,'S1'!$B$6:$B$32,$A79,'S1'!$E$6:$E$32,"Víctor")+SUMIFS('S1'!$I$6:$I$32,'S1'!$B$6:$B$32,$A79,'S1'!$E$6:$E$32,"Ambos")+SUMIFS('S2'!$I$6:$I$23,'S2'!$B$6:$B$23,$A79,'S2'!$E$6:$E$23,"Víctor")+SUMIFS('S2'!$I$6:$I$23,'S2'!$B$6:$B$23,$A79,'S2'!$E$6:$E$23,"Ambos")+SUMIFS('S3'!$I$6:$I$19,'S3'!$B$6:$B$19,$A79,'S3'!$E$6:$E$19,"Víctor")+SUMIFS('S3'!$I$6:$I$19,'S3'!$B$6:$B$19,$A79,'S3'!$E$6:$E$19,"Ambos")+SUMIFS('S4'!$I$6:$I$20,'S4'!$B$6:$B$20,$A79,'S4'!$E$6:$E$20,"Víctor")+SUMIFS('S4'!$I$6:$I$20,'S4'!$B$6:$B$20,$A79,'S4'!$E$6:$E$20,"Ambos")+SUMIFS('S5'!$I$6:$I$20,'S5'!$B$6:$B$20,$A79,'S5'!$E$6:$E$20,"Víctor")+SUMIFS('S5'!$I$6:$I$20,'S5'!$B$6:$B$20,$A79,'S5'!$E$6:$E$20,"Ambos")+SUMIFS('S6'!$I$6:$I$17,'S6'!$B$6:$B$17,$A79,'S6'!$E$6:$E$17,"Víctor")+SUMIFS('S6'!$I$6:$I$17,'S6'!$B$6:$B$17,$A79,'S6'!$E$6:$E$17,"Ambos")+SUMIFS('S7'!$I$6:$I$19,'S7'!$B$6:$B$19,$A79,'S7'!$E$6:$E$19,"Víctor")+SUMIFS('S7'!$I$6:$I$19,'S7'!$B$6:$B$19,$A79,'S7'!$E$6:$E$19,"Ambos")+SUMIFS('S8'!$I$6:$I$23,'S8'!$B$6:$B$23,$A79,'S8'!$E$6:$E$23,"Víctor")+SUMIFS('S8'!$I$6:$I$23,'S8'!$B$6:$B$23,$A79,'S8'!$E$6:$E$23,"Ambos")+SUMIFS('S9'!$I$6:$I$15,'S9'!$B$6:$B$15,$A79,'S9'!$E$6:$E$15,"Víctor")+SUMIFS('S9'!$I$6:$I$15,'S9'!$B$6:$B$15,$A79,'S9'!$E$6:$E$15,"Ambos")+SUMIFS('S10'!$I$6:$I$13,'S10'!$B$6:$B$13,$A79,'S10'!$E$6:$E$13,"Víctor")+SUMIFS('S10'!$I$6:$I$13,'S10'!$B$6:$B$13,$A79,'S10'!$E$6:$E$13,"Ambos")+SUMIFS('Holgura'!$I$6:$I$11,'Holgura'!$B$6:$B$11,$A79,'Holgura'!$E$6:$E$11,"Víctor")+SUMIFS('Holgura'!$I$6:$I$11,'Holgura'!$B$6:$B$11,$A79,'Holgura'!$E$6:$E$11,"Ambos")+SUMIFS('Entrega'!$I$6:$I$9,'Entrega'!$B$6:$B$9,$A79,'Entrega'!$E$6:$E$9,"Víctor")+SUMIFS('Entrega'!$I$6:$I$9,'Entrega'!$B$6:$B$9,$A79,'Entrega'!$E$6:$E$9,"Ambos")+SUMIFS('Defensa'!$I$6:$I$10,'Defensa'!$B$6:$B$10,$A79,'Defensa'!$E$6:$E$10,"Víctor")+SUMIFS('Defensa'!$I$6:$I$10,'Defensa'!$B$6:$B$10,$A79,'Defensa'!$E$6:$E$10,"Ambos")</f>
+        <f>SUMIFS('S1'!$I$6:$I$32,'S1'!$B$6:$B$32,$A79,'S1'!$E$6:$E$32,"Víctor")+SUMIFS('S1'!$I$6:$I$32,'S1'!$B$6:$B$32,$A79,'S1'!$E$6:$E$32,"Ambos")+SUMIFS('S2'!$I$6:$I$23,'S2'!$B$6:$B$23,$A79,'S2'!$E$6:$E$23,"Víctor")+SUMIFS('S2'!$I$6:$I$23,'S2'!$B$6:$B$23,$A79,'S2'!$E$6:$E$23,"Ambos")+SUMIFS('S3'!$I$6:$I$24,'S3'!$B$6:$B$24,$A79,'S3'!$E$6:$E$24,"Víctor")+SUMIFS('S3'!$I$6:$I$24,'S3'!$B$6:$B$24,$A79,'S3'!$E$6:$E$24,"Ambos")+SUMIFS('S4'!$I$6:$I$22,'S4'!$B$6:$B$22,$A79,'S4'!$E$6:$E$22,"Víctor")+SUMIFS('S4'!$I$6:$I$22,'S4'!$B$6:$B$22,$A79,'S4'!$E$6:$E$22,"Ambos")+SUMIFS('S5'!$I$6:$I$20,'S5'!$B$6:$B$20,$A79,'S5'!$E$6:$E$20,"Víctor")+SUMIFS('S5'!$I$6:$I$20,'S5'!$B$6:$B$20,$A79,'S5'!$E$6:$E$20,"Ambos")+SUMIFS('S6'!$I$6:$I$17,'S6'!$B$6:$B$17,$A79,'S6'!$E$6:$E$17,"Víctor")+SUMIFS('S6'!$I$6:$I$17,'S6'!$B$6:$B$17,$A79,'S6'!$E$6:$E$17,"Ambos")+SUMIFS('S7'!$I$6:$I$19,'S7'!$B$6:$B$19,$A79,'S7'!$E$6:$E$19,"Víctor")+SUMIFS('S7'!$I$6:$I$19,'S7'!$B$6:$B$19,$A79,'S7'!$E$6:$E$19,"Ambos")+SUMIFS('S8'!$I$6:$I$23,'S8'!$B$6:$B$23,$A79,'S8'!$E$6:$E$23,"Víctor")+SUMIFS('S8'!$I$6:$I$23,'S8'!$B$6:$B$23,$A79,'S8'!$E$6:$E$23,"Ambos")+SUMIFS('S9'!$I$6:$I$15,'S9'!$B$6:$B$15,$A79,'S9'!$E$6:$E$15,"Víctor")+SUMIFS('S9'!$I$6:$I$15,'S9'!$B$6:$B$15,$A79,'S9'!$E$6:$E$15,"Ambos")+SUMIFS('S10'!$I$6:$I$13,'S10'!$B$6:$B$13,$A79,'S10'!$E$6:$E$13,"Víctor")+SUMIFS('S10'!$I$6:$I$13,'S10'!$B$6:$B$13,$A79,'S10'!$E$6:$E$13,"Ambos")+SUMIFS('Holgura'!$I$6:$I$11,'Holgura'!$B$6:$B$11,$A79,'Holgura'!$E$6:$E$11,"Víctor")+SUMIFS('Holgura'!$I$6:$I$11,'Holgura'!$B$6:$B$11,$A79,'Holgura'!$E$6:$E$11,"Ambos")+SUMIFS('Entrega'!$I$6:$I$9,'Entrega'!$B$6:$B$9,$A79,'Entrega'!$E$6:$E$9,"Víctor")+SUMIFS('Entrega'!$I$6:$I$9,'Entrega'!$B$6:$B$9,$A79,'Entrega'!$E$6:$E$9,"Ambos")+SUMIFS('Defensa'!$I$6:$I$10,'Defensa'!$B$6:$B$10,$A79,'Defensa'!$E$6:$E$10,"Víctor")+SUMIFS('Defensa'!$I$6:$I$10,'Defensa'!$B$6:$B$10,$A79,'Defensa'!$E$6:$E$10,"Ambos")</f>
         <v/>
       </c>
       <c r="E79" s="21">
-        <f>SUMIFS('S1'!$I$6:$I$32,'S1'!$B$6:$B$32,$A79,'S1'!$E$6:$E$32,"Diego")+SUMIFS('S1'!$I$6:$I$32,'S1'!$B$6:$B$32,$A79,'S1'!$E$6:$E$32,"Ambos")+SUMIFS('S2'!$I$6:$I$23,'S2'!$B$6:$B$23,$A79,'S2'!$E$6:$E$23,"Diego")+SUMIFS('S2'!$I$6:$I$23,'S2'!$B$6:$B$23,$A79,'S2'!$E$6:$E$23,"Ambos")+SUMIFS('S3'!$I$6:$I$19,'S3'!$B$6:$B$19,$A79,'S3'!$E$6:$E$19,"Diego")+SUMIFS('S3'!$I$6:$I$19,'S3'!$B$6:$B$19,$A79,'S3'!$E$6:$E$19,"Ambos")+SUMIFS('S4'!$I$6:$I$20,'S4'!$B$6:$B$20,$A79,'S4'!$E$6:$E$20,"Diego")+SUMIFS('S4'!$I$6:$I$20,'S4'!$B$6:$B$20,$A79,'S4'!$E$6:$E$20,"Ambos")+SUMIFS('S5'!$I$6:$I$20,'S5'!$B$6:$B$20,$A79,'S5'!$E$6:$E$20,"Diego")+SUMIFS('S5'!$I$6:$I$20,'S5'!$B$6:$B$20,$A79,'S5'!$E$6:$E$20,"Ambos")+SUMIFS('S6'!$I$6:$I$17,'S6'!$B$6:$B$17,$A79,'S6'!$E$6:$E$17,"Diego")+SUMIFS('S6'!$I$6:$I$17,'S6'!$B$6:$B$17,$A79,'S6'!$E$6:$E$17,"Ambos")+SUMIFS('S7'!$I$6:$I$19,'S7'!$B$6:$B$19,$A79,'S7'!$E$6:$E$19,"Diego")+SUMIFS('S7'!$I$6:$I$19,'S7'!$B$6:$B$19,$A79,'S7'!$E$6:$E$19,"Ambos")+SUMIFS('S8'!$I$6:$I$23,'S8'!$B$6:$B$23,$A79,'S8'!$E$6:$E$23,"Diego")+SUMIFS('S8'!$I$6:$I$23,'S8'!$B$6:$B$23,$A79,'S8'!$E$6:$E$23,"Ambos")+SUMIFS('S9'!$I$6:$I$15,'S9'!$B$6:$B$15,$A79,'S9'!$E$6:$E$15,"Diego")+SUMIFS('S9'!$I$6:$I$15,'S9'!$B$6:$B$15,$A79,'S9'!$E$6:$E$15,"Ambos")+SUMIFS('S10'!$I$6:$I$13,'S10'!$B$6:$B$13,$A79,'S10'!$E$6:$E$13,"Diego")+SUMIFS('S10'!$I$6:$I$13,'S10'!$B$6:$B$13,$A79,'S10'!$E$6:$E$13,"Ambos")+SUMIFS('Holgura'!$I$6:$I$11,'Holgura'!$B$6:$B$11,$A79,'Holgura'!$E$6:$E$11,"Diego")+SUMIFS('Holgura'!$I$6:$I$11,'Holgura'!$B$6:$B$11,$A79,'Holgura'!$E$6:$E$11,"Ambos")+SUMIFS('Entrega'!$I$6:$I$9,'Entrega'!$B$6:$B$9,$A79,'Entrega'!$E$6:$E$9,"Diego")+SUMIFS('Entrega'!$I$6:$I$9,'Entrega'!$B$6:$B$9,$A79,'Entrega'!$E$6:$E$9,"Ambos")+SUMIFS('Defensa'!$I$6:$I$10,'Defensa'!$B$6:$B$10,$A79,'Defensa'!$E$6:$E$10,"Diego")+SUMIFS('Defensa'!$I$6:$I$10,'Defensa'!$B$6:$B$10,$A79,'Defensa'!$E$6:$E$10,"Ambos")</f>
+        <f>SUMIFS('S1'!$I$6:$I$32,'S1'!$B$6:$B$32,$A79,'S1'!$E$6:$E$32,"Diego")+SUMIFS('S1'!$I$6:$I$32,'S1'!$B$6:$B$32,$A79,'S1'!$E$6:$E$32,"Ambos")+SUMIFS('S2'!$I$6:$I$23,'S2'!$B$6:$B$23,$A79,'S2'!$E$6:$E$23,"Diego")+SUMIFS('S2'!$I$6:$I$23,'S2'!$B$6:$B$23,$A79,'S2'!$E$6:$E$23,"Ambos")+SUMIFS('S3'!$I$6:$I$24,'S3'!$B$6:$B$24,$A79,'S3'!$E$6:$E$24,"Diego")+SUMIFS('S3'!$I$6:$I$24,'S3'!$B$6:$B$24,$A79,'S3'!$E$6:$E$24,"Ambos")+SUMIFS('S4'!$I$6:$I$22,'S4'!$B$6:$B$22,$A79,'S4'!$E$6:$E$22,"Diego")+SUMIFS('S4'!$I$6:$I$22,'S4'!$B$6:$B$22,$A79,'S4'!$E$6:$E$22,"Ambos")+SUMIFS('S5'!$I$6:$I$20,'S5'!$B$6:$B$20,$A79,'S5'!$E$6:$E$20,"Diego")+SUMIFS('S5'!$I$6:$I$20,'S5'!$B$6:$B$20,$A79,'S5'!$E$6:$E$20,"Ambos")+SUMIFS('S6'!$I$6:$I$17,'S6'!$B$6:$B$17,$A79,'S6'!$E$6:$E$17,"Diego")+SUMIFS('S6'!$I$6:$I$17,'S6'!$B$6:$B$17,$A79,'S6'!$E$6:$E$17,"Ambos")+SUMIFS('S7'!$I$6:$I$19,'S7'!$B$6:$B$19,$A79,'S7'!$E$6:$E$19,"Diego")+SUMIFS('S7'!$I$6:$I$19,'S7'!$B$6:$B$19,$A79,'S7'!$E$6:$E$19,"Ambos")+SUMIFS('S8'!$I$6:$I$23,'S8'!$B$6:$B$23,$A79,'S8'!$E$6:$E$23,"Diego")+SUMIFS('S8'!$I$6:$I$23,'S8'!$B$6:$B$23,$A79,'S8'!$E$6:$E$23,"Ambos")+SUMIFS('S9'!$I$6:$I$15,'S9'!$B$6:$B$15,$A79,'S9'!$E$6:$E$15,"Diego")+SUMIFS('S9'!$I$6:$I$15,'S9'!$B$6:$B$15,$A79,'S9'!$E$6:$E$15,"Ambos")+SUMIFS('S10'!$I$6:$I$13,'S10'!$B$6:$B$13,$A79,'S10'!$E$6:$E$13,"Diego")+SUMIFS('S10'!$I$6:$I$13,'S10'!$B$6:$B$13,$A79,'S10'!$E$6:$E$13,"Ambos")+SUMIFS('Holgura'!$I$6:$I$11,'Holgura'!$B$6:$B$11,$A79,'Holgura'!$E$6:$E$11,"Diego")+SUMIFS('Holgura'!$I$6:$I$11,'Holgura'!$B$6:$B$11,$A79,'Holgura'!$E$6:$E$11,"Ambos")+SUMIFS('Entrega'!$I$6:$I$9,'Entrega'!$B$6:$B$9,$A79,'Entrega'!$E$6:$E$9,"Diego")+SUMIFS('Entrega'!$I$6:$I$9,'Entrega'!$B$6:$B$9,$A79,'Entrega'!$E$6:$E$9,"Ambos")+SUMIFS('Defensa'!$I$6:$I$10,'Defensa'!$B$6:$B$10,$A79,'Defensa'!$E$6:$E$10,"Diego")+SUMIFS('Defensa'!$I$6:$I$10,'Defensa'!$B$6:$B$10,$A79,'Defensa'!$E$6:$E$10,"Ambos")</f>
         <v/>
       </c>
       <c r="F79" s="21">
-        <f>COUNTIFS('S1'!$B$6:$B$32,$A79,'S1'!$E$6:$E$32,"Víctor")+COUNTIFS('S1'!$B$6:$B$32,$A79,'S1'!$E$6:$E$32,"Ambos")+COUNTIFS('S2'!$B$6:$B$23,$A79,'S2'!$E$6:$E$23,"Víctor")+COUNTIFS('S2'!$B$6:$B$23,$A79,'S2'!$E$6:$E$23,"Ambos")+COUNTIFS('S3'!$B$6:$B$19,$A79,'S3'!$E$6:$E$19,"Víctor")+COUNTIFS('S3'!$B$6:$B$19,$A79,'S3'!$E$6:$E$19,"Ambos")+COUNTIFS('S4'!$B$6:$B$20,$A79,'S4'!$E$6:$E$20,"Víctor")+COUNTIFS('S4'!$B$6:$B$20,$A79,'S4'!$E$6:$E$20,"Ambos")+COUNTIFS('S5'!$B$6:$B$20,$A79,'S5'!$E$6:$E$20,"Víctor")+COUNTIFS('S5'!$B$6:$B$20,$A79,'S5'!$E$6:$E$20,"Ambos")+COUNTIFS('S6'!$B$6:$B$17,$A79,'S6'!$E$6:$E$17,"Víctor")+COUNTIFS('S6'!$B$6:$B$17,$A79,'S6'!$E$6:$E$17,"Ambos")+COUNTIFS('S7'!$B$6:$B$19,$A79,'S7'!$E$6:$E$19,"Víctor")+COUNTIFS('S7'!$B$6:$B$19,$A79,'S7'!$E$6:$E$19,"Ambos")+COUNTIFS('S8'!$B$6:$B$23,$A79,'S8'!$E$6:$E$23,"Víctor")+COUNTIFS('S8'!$B$6:$B$23,$A79,'S8'!$E$6:$E$23,"Ambos")+COUNTIFS('S9'!$B$6:$B$15,$A79,'S9'!$E$6:$E$15,"Víctor")+COUNTIFS('S9'!$B$6:$B$15,$A79,'S9'!$E$6:$E$15,"Ambos")+COUNTIFS('S10'!$B$6:$B$13,$A79,'S10'!$E$6:$E$13,"Víctor")+COUNTIFS('S10'!$B$6:$B$13,$A79,'S10'!$E$6:$E$13,"Ambos")+COUNTIFS('Holgura'!$B$6:$B$11,$A79,'Holgura'!$E$6:$E$11,"Víctor")+COUNTIFS('Holgura'!$B$6:$B$11,$A79,'Holgura'!$E$6:$E$11,"Ambos")+COUNTIFS('Entrega'!$B$6:$B$9,$A79,'Entrega'!$E$6:$E$9,"Víctor")+COUNTIFS('Entrega'!$B$6:$B$9,$A79,'Entrega'!$E$6:$E$9,"Ambos")+COUNTIFS('Defensa'!$B$6:$B$10,$A79,'Defensa'!$E$6:$E$10,"Víctor")+COUNTIFS('Defensa'!$B$6:$B$10,$A79,'Defensa'!$E$6:$E$10,"Ambos")</f>
+        <f>COUNTIFS('S1'!$B$6:$B$32,$A79,'S1'!$E$6:$E$32,"Víctor")+COUNTIFS('S1'!$B$6:$B$32,$A79,'S1'!$E$6:$E$32,"Ambos")+COUNTIFS('S2'!$B$6:$B$23,$A79,'S2'!$E$6:$E$23,"Víctor")+COUNTIFS('S2'!$B$6:$B$23,$A79,'S2'!$E$6:$E$23,"Ambos")+COUNTIFS('S3'!$B$6:$B$24,$A79,'S3'!$E$6:$E$24,"Víctor")+COUNTIFS('S3'!$B$6:$B$24,$A79,'S3'!$E$6:$E$24,"Ambos")+COUNTIFS('S4'!$B$6:$B$22,$A79,'S4'!$E$6:$E$22,"Víctor")+COUNTIFS('S4'!$B$6:$B$22,$A79,'S4'!$E$6:$E$22,"Ambos")+COUNTIFS('S5'!$B$6:$B$20,$A79,'S5'!$E$6:$E$20,"Víctor")+COUNTIFS('S5'!$B$6:$B$20,$A79,'S5'!$E$6:$E$20,"Ambos")+COUNTIFS('S6'!$B$6:$B$17,$A79,'S6'!$E$6:$E$17,"Víctor")+COUNTIFS('S6'!$B$6:$B$17,$A79,'S6'!$E$6:$E$17,"Ambos")+COUNTIFS('S7'!$B$6:$B$19,$A79,'S7'!$E$6:$E$19,"Víctor")+COUNTIFS('S7'!$B$6:$B$19,$A79,'S7'!$E$6:$E$19,"Ambos")+COUNTIFS('S8'!$B$6:$B$23,$A79,'S8'!$E$6:$E$23,"Víctor")+COUNTIFS('S8'!$B$6:$B$23,$A79,'S8'!$E$6:$E$23,"Ambos")+COUNTIFS('S9'!$B$6:$B$15,$A79,'S9'!$E$6:$E$15,"Víctor")+COUNTIFS('S9'!$B$6:$B$15,$A79,'S9'!$E$6:$E$15,"Ambos")+COUNTIFS('S10'!$B$6:$B$13,$A79,'S10'!$E$6:$E$13,"Víctor")+COUNTIFS('S10'!$B$6:$B$13,$A79,'S10'!$E$6:$E$13,"Ambos")+COUNTIFS('Holgura'!$B$6:$B$11,$A79,'Holgura'!$E$6:$E$11,"Víctor")+COUNTIFS('Holgura'!$B$6:$B$11,$A79,'Holgura'!$E$6:$E$11,"Ambos")+COUNTIFS('Entrega'!$B$6:$B$9,$A79,'Entrega'!$E$6:$E$9,"Víctor")+COUNTIFS('Entrega'!$B$6:$B$9,$A79,'Entrega'!$E$6:$E$9,"Ambos")+COUNTIFS('Defensa'!$B$6:$B$10,$A79,'Defensa'!$E$6:$E$10,"Víctor")+COUNTIFS('Defensa'!$B$6:$B$10,$A79,'Defensa'!$E$6:$E$10,"Ambos")</f>
         <v/>
       </c>
       <c r="G79" s="21">
-        <f>COUNTIFS('S1'!$B$6:$B$32,$A79,'S1'!$E$6:$E$32,"Diego")+COUNTIFS('S1'!$B$6:$B$32,$A79,'S1'!$E$6:$E$32,"Ambos")+COUNTIFS('S2'!$B$6:$B$23,$A79,'S2'!$E$6:$E$23,"Diego")+COUNTIFS('S2'!$B$6:$B$23,$A79,'S2'!$E$6:$E$23,"Ambos")+COUNTIFS('S3'!$B$6:$B$19,$A79,'S3'!$E$6:$E$19,"Diego")+COUNTIFS('S3'!$B$6:$B$19,$A79,'S3'!$E$6:$E$19,"Ambos")+COUNTIFS('S4'!$B$6:$B$20,$A79,'S4'!$E$6:$E$20,"Diego")+COUNTIFS('S4'!$B$6:$B$20,$A79,'S4'!$E$6:$E$20,"Ambos")+COUNTIFS('S5'!$B$6:$B$20,$A79,'S5'!$E$6:$E$20,"Diego")+COUNTIFS('S5'!$B$6:$B$20,$A79,'S5'!$E$6:$E$20,"Ambos")+COUNTIFS('S6'!$B$6:$B$17,$A79,'S6'!$E$6:$E$17,"Diego")+COUNTIFS('S6'!$B$6:$B$17,$A79,'S6'!$E$6:$E$17,"Ambos")+COUNTIFS('S7'!$B$6:$B$19,$A79,'S7'!$E$6:$E$19,"Diego")+COUNTIFS('S7'!$B$6:$B$19,$A79,'S7'!$E$6:$E$19,"Ambos")+COUNTIFS('S8'!$B$6:$B$23,$A79,'S8'!$E$6:$E$23,"Diego")+COUNTIFS('S8'!$B$6:$B$23,$A79,'S8'!$E$6:$E$23,"Ambos")+COUNTIFS('S9'!$B$6:$B$15,$A79,'S9'!$E$6:$E$15,"Diego")+COUNTIFS('S9'!$B$6:$B$15,$A79,'S9'!$E$6:$E$15,"Ambos")+COUNTIFS('S10'!$B$6:$B$13,$A79,'S10'!$E$6:$E$13,"Diego")+COUNTIFS('S10'!$B$6:$B$13,$A79,'S10'!$E$6:$E$13,"Ambos")+COUNTIFS('Holgura'!$B$6:$B$11,$A79,'Holgura'!$E$6:$E$11,"Diego")+COUNTIFS('Holgura'!$B$6:$B$11,$A79,'Holgura'!$E$6:$E$11,"Ambos")+COUNTIFS('Entrega'!$B$6:$B$9,$A79,'Entrega'!$E$6:$E$9,"Diego")+COUNTIFS('Entrega'!$B$6:$B$9,$A79,'Entrega'!$E$6:$E$9,"Ambos")+COUNTIFS('Defensa'!$B$6:$B$10,$A79,'Defensa'!$E$6:$E$10,"Diego")+COUNTIFS('Defensa'!$B$6:$B$10,$A79,'Defensa'!$E$6:$E$10,"Ambos")</f>
+        <f>COUNTIFS('S1'!$B$6:$B$32,$A79,'S1'!$E$6:$E$32,"Diego")+COUNTIFS('S1'!$B$6:$B$32,$A79,'S1'!$E$6:$E$32,"Ambos")+COUNTIFS('S2'!$B$6:$B$23,$A79,'S2'!$E$6:$E$23,"Diego")+COUNTIFS('S2'!$B$6:$B$23,$A79,'S2'!$E$6:$E$23,"Ambos")+COUNTIFS('S3'!$B$6:$B$24,$A79,'S3'!$E$6:$E$24,"Diego")+COUNTIFS('S3'!$B$6:$B$24,$A79,'S3'!$E$6:$E$24,"Ambos")+COUNTIFS('S4'!$B$6:$B$22,$A79,'S4'!$E$6:$E$22,"Diego")+COUNTIFS('S4'!$B$6:$B$22,$A79,'S4'!$E$6:$E$22,"Ambos")+COUNTIFS('S5'!$B$6:$B$20,$A79,'S5'!$E$6:$E$20,"Diego")+COUNTIFS('S5'!$B$6:$B$20,$A79,'S5'!$E$6:$E$20,"Ambos")+COUNTIFS('S6'!$B$6:$B$17,$A79,'S6'!$E$6:$E$17,"Diego")+COUNTIFS('S6'!$B$6:$B$17,$A79,'S6'!$E$6:$E$17,"Ambos")+COUNTIFS('S7'!$B$6:$B$19,$A79,'S7'!$E$6:$E$19,"Diego")+COUNTIFS('S7'!$B$6:$B$19,$A79,'S7'!$E$6:$E$19,"Ambos")+COUNTIFS('S8'!$B$6:$B$23,$A79,'S8'!$E$6:$E$23,"Diego")+COUNTIFS('S8'!$B$6:$B$23,$A79,'S8'!$E$6:$E$23,"Ambos")+COUNTIFS('S9'!$B$6:$B$15,$A79,'S9'!$E$6:$E$15,"Diego")+COUNTIFS('S9'!$B$6:$B$15,$A79,'S9'!$E$6:$E$15,"Ambos")+COUNTIFS('S10'!$B$6:$B$13,$A79,'S10'!$E$6:$E$13,"Diego")+COUNTIFS('S10'!$B$6:$B$13,$A79,'S10'!$E$6:$E$13,"Ambos")+COUNTIFS('Holgura'!$B$6:$B$11,$A79,'Holgura'!$E$6:$E$11,"Diego")+COUNTIFS('Holgura'!$B$6:$B$11,$A79,'Holgura'!$E$6:$E$11,"Ambos")+COUNTIFS('Entrega'!$B$6:$B$9,$A79,'Entrega'!$E$6:$E$9,"Diego")+COUNTIFS('Entrega'!$B$6:$B$9,$A79,'Entrega'!$E$6:$E$9,"Ambos")+COUNTIFS('Defensa'!$B$6:$B$10,$A79,'Defensa'!$E$6:$E$10,"Diego")+COUNTIFS('Defensa'!$B$6:$B$10,$A79,'Defensa'!$E$6:$E$10,"Ambos")</f>
         <v/>
       </c>
     </row>
@@ -10855,19 +10876,19 @@
         <v/>
       </c>
       <c r="D80" s="21">
-        <f>SUMIFS('S1'!$I$6:$I$32,'S1'!$B$6:$B$32,$A80,'S1'!$E$6:$E$32,"Víctor")+SUMIFS('S1'!$I$6:$I$32,'S1'!$B$6:$B$32,$A80,'S1'!$E$6:$E$32,"Ambos")+SUMIFS('S2'!$I$6:$I$23,'S2'!$B$6:$B$23,$A80,'S2'!$E$6:$E$23,"Víctor")+SUMIFS('S2'!$I$6:$I$23,'S2'!$B$6:$B$23,$A80,'S2'!$E$6:$E$23,"Ambos")+SUMIFS('S3'!$I$6:$I$19,'S3'!$B$6:$B$19,$A80,'S3'!$E$6:$E$19,"Víctor")+SUMIFS('S3'!$I$6:$I$19,'S3'!$B$6:$B$19,$A80,'S3'!$E$6:$E$19,"Ambos")+SUMIFS('S4'!$I$6:$I$20,'S4'!$B$6:$B$20,$A80,'S4'!$E$6:$E$20,"Víctor")+SUMIFS('S4'!$I$6:$I$20,'S4'!$B$6:$B$20,$A80,'S4'!$E$6:$E$20,"Ambos")+SUMIFS('S5'!$I$6:$I$20,'S5'!$B$6:$B$20,$A80,'S5'!$E$6:$E$20,"Víctor")+SUMIFS('S5'!$I$6:$I$20,'S5'!$B$6:$B$20,$A80,'S5'!$E$6:$E$20,"Ambos")+SUMIFS('S6'!$I$6:$I$17,'S6'!$B$6:$B$17,$A80,'S6'!$E$6:$E$17,"Víctor")+SUMIFS('S6'!$I$6:$I$17,'S6'!$B$6:$B$17,$A80,'S6'!$E$6:$E$17,"Ambos")+SUMIFS('S7'!$I$6:$I$19,'S7'!$B$6:$B$19,$A80,'S7'!$E$6:$E$19,"Víctor")+SUMIFS('S7'!$I$6:$I$19,'S7'!$B$6:$B$19,$A80,'S7'!$E$6:$E$19,"Ambos")+SUMIFS('S8'!$I$6:$I$23,'S8'!$B$6:$B$23,$A80,'S8'!$E$6:$E$23,"Víctor")+SUMIFS('S8'!$I$6:$I$23,'S8'!$B$6:$B$23,$A80,'S8'!$E$6:$E$23,"Ambos")+SUMIFS('S9'!$I$6:$I$15,'S9'!$B$6:$B$15,$A80,'S9'!$E$6:$E$15,"Víctor")+SUMIFS('S9'!$I$6:$I$15,'S9'!$B$6:$B$15,$A80,'S9'!$E$6:$E$15,"Ambos")+SUMIFS('S10'!$I$6:$I$13,'S10'!$B$6:$B$13,$A80,'S10'!$E$6:$E$13,"Víctor")+SUMIFS('S10'!$I$6:$I$13,'S10'!$B$6:$B$13,$A80,'S10'!$E$6:$E$13,"Ambos")+SUMIFS('Holgura'!$I$6:$I$11,'Holgura'!$B$6:$B$11,$A80,'Holgura'!$E$6:$E$11,"Víctor")+SUMIFS('Holgura'!$I$6:$I$11,'Holgura'!$B$6:$B$11,$A80,'Holgura'!$E$6:$E$11,"Ambos")+SUMIFS('Entrega'!$I$6:$I$9,'Entrega'!$B$6:$B$9,$A80,'Entrega'!$E$6:$E$9,"Víctor")+SUMIFS('Entrega'!$I$6:$I$9,'Entrega'!$B$6:$B$9,$A80,'Entrega'!$E$6:$E$9,"Ambos")+SUMIFS('Defensa'!$I$6:$I$10,'Defensa'!$B$6:$B$10,$A80,'Defensa'!$E$6:$E$10,"Víctor")+SUMIFS('Defensa'!$I$6:$I$10,'Defensa'!$B$6:$B$10,$A80,'Defensa'!$E$6:$E$10,"Ambos")</f>
+        <f>SUMIFS('S1'!$I$6:$I$32,'S1'!$B$6:$B$32,$A80,'S1'!$E$6:$E$32,"Víctor")+SUMIFS('S1'!$I$6:$I$32,'S1'!$B$6:$B$32,$A80,'S1'!$E$6:$E$32,"Ambos")+SUMIFS('S2'!$I$6:$I$23,'S2'!$B$6:$B$23,$A80,'S2'!$E$6:$E$23,"Víctor")+SUMIFS('S2'!$I$6:$I$23,'S2'!$B$6:$B$23,$A80,'S2'!$E$6:$E$23,"Ambos")+SUMIFS('S3'!$I$6:$I$24,'S3'!$B$6:$B$24,$A80,'S3'!$E$6:$E$24,"Víctor")+SUMIFS('S3'!$I$6:$I$24,'S3'!$B$6:$B$24,$A80,'S3'!$E$6:$E$24,"Ambos")+SUMIFS('S4'!$I$6:$I$22,'S4'!$B$6:$B$22,$A80,'S4'!$E$6:$E$22,"Víctor")+SUMIFS('S4'!$I$6:$I$22,'S4'!$B$6:$B$22,$A80,'S4'!$E$6:$E$22,"Ambos")+SUMIFS('S5'!$I$6:$I$20,'S5'!$B$6:$B$20,$A80,'S5'!$E$6:$E$20,"Víctor")+SUMIFS('S5'!$I$6:$I$20,'S5'!$B$6:$B$20,$A80,'S5'!$E$6:$E$20,"Ambos")+SUMIFS('S6'!$I$6:$I$17,'S6'!$B$6:$B$17,$A80,'S6'!$E$6:$E$17,"Víctor")+SUMIFS('S6'!$I$6:$I$17,'S6'!$B$6:$B$17,$A80,'S6'!$E$6:$E$17,"Ambos")+SUMIFS('S7'!$I$6:$I$19,'S7'!$B$6:$B$19,$A80,'S7'!$E$6:$E$19,"Víctor")+SUMIFS('S7'!$I$6:$I$19,'S7'!$B$6:$B$19,$A80,'S7'!$E$6:$E$19,"Ambos")+SUMIFS('S8'!$I$6:$I$23,'S8'!$B$6:$B$23,$A80,'S8'!$E$6:$E$23,"Víctor")+SUMIFS('S8'!$I$6:$I$23,'S8'!$B$6:$B$23,$A80,'S8'!$E$6:$E$23,"Ambos")+SUMIFS('S9'!$I$6:$I$15,'S9'!$B$6:$B$15,$A80,'S9'!$E$6:$E$15,"Víctor")+SUMIFS('S9'!$I$6:$I$15,'S9'!$B$6:$B$15,$A80,'S9'!$E$6:$E$15,"Ambos")+SUMIFS('S10'!$I$6:$I$13,'S10'!$B$6:$B$13,$A80,'S10'!$E$6:$E$13,"Víctor")+SUMIFS('S10'!$I$6:$I$13,'S10'!$B$6:$B$13,$A80,'S10'!$E$6:$E$13,"Ambos")+SUMIFS('Holgura'!$I$6:$I$11,'Holgura'!$B$6:$B$11,$A80,'Holgura'!$E$6:$E$11,"Víctor")+SUMIFS('Holgura'!$I$6:$I$11,'Holgura'!$B$6:$B$11,$A80,'Holgura'!$E$6:$E$11,"Ambos")+SUMIFS('Entrega'!$I$6:$I$9,'Entrega'!$B$6:$B$9,$A80,'Entrega'!$E$6:$E$9,"Víctor")+SUMIFS('Entrega'!$I$6:$I$9,'Entrega'!$B$6:$B$9,$A80,'Entrega'!$E$6:$E$9,"Ambos")+SUMIFS('Defensa'!$I$6:$I$10,'Defensa'!$B$6:$B$10,$A80,'Defensa'!$E$6:$E$10,"Víctor")+SUMIFS('Defensa'!$I$6:$I$10,'Defensa'!$B$6:$B$10,$A80,'Defensa'!$E$6:$E$10,"Ambos")</f>
         <v/>
       </c>
       <c r="E80" s="21">
-        <f>SUMIFS('S1'!$I$6:$I$32,'S1'!$B$6:$B$32,$A80,'S1'!$E$6:$E$32,"Diego")+SUMIFS('S1'!$I$6:$I$32,'S1'!$B$6:$B$32,$A80,'S1'!$E$6:$E$32,"Ambos")+SUMIFS('S2'!$I$6:$I$23,'S2'!$B$6:$B$23,$A80,'S2'!$E$6:$E$23,"Diego")+SUMIFS('S2'!$I$6:$I$23,'S2'!$B$6:$B$23,$A80,'S2'!$E$6:$E$23,"Ambos")+SUMIFS('S3'!$I$6:$I$19,'S3'!$B$6:$B$19,$A80,'S3'!$E$6:$E$19,"Diego")+SUMIFS('S3'!$I$6:$I$19,'S3'!$B$6:$B$19,$A80,'S3'!$E$6:$E$19,"Ambos")+SUMIFS('S4'!$I$6:$I$20,'S4'!$B$6:$B$20,$A80,'S4'!$E$6:$E$20,"Diego")+SUMIFS('S4'!$I$6:$I$20,'S4'!$B$6:$B$20,$A80,'S4'!$E$6:$E$20,"Ambos")+SUMIFS('S5'!$I$6:$I$20,'S5'!$B$6:$B$20,$A80,'S5'!$E$6:$E$20,"Diego")+SUMIFS('S5'!$I$6:$I$20,'S5'!$B$6:$B$20,$A80,'S5'!$E$6:$E$20,"Ambos")+SUMIFS('S6'!$I$6:$I$17,'S6'!$B$6:$B$17,$A80,'S6'!$E$6:$E$17,"Diego")+SUMIFS('S6'!$I$6:$I$17,'S6'!$B$6:$B$17,$A80,'S6'!$E$6:$E$17,"Ambos")+SUMIFS('S7'!$I$6:$I$19,'S7'!$B$6:$B$19,$A80,'S7'!$E$6:$E$19,"Diego")+SUMIFS('S7'!$I$6:$I$19,'S7'!$B$6:$B$19,$A80,'S7'!$E$6:$E$19,"Ambos")+SUMIFS('S8'!$I$6:$I$23,'S8'!$B$6:$B$23,$A80,'S8'!$E$6:$E$23,"Diego")+SUMIFS('S8'!$I$6:$I$23,'S8'!$B$6:$B$23,$A80,'S8'!$E$6:$E$23,"Ambos")+SUMIFS('S9'!$I$6:$I$15,'S9'!$B$6:$B$15,$A80,'S9'!$E$6:$E$15,"Diego")+SUMIFS('S9'!$I$6:$I$15,'S9'!$B$6:$B$15,$A80,'S9'!$E$6:$E$15,"Ambos")+SUMIFS('S10'!$I$6:$I$13,'S10'!$B$6:$B$13,$A80,'S10'!$E$6:$E$13,"Diego")+SUMIFS('S10'!$I$6:$I$13,'S10'!$B$6:$B$13,$A80,'S10'!$E$6:$E$13,"Ambos")+SUMIFS('Holgura'!$I$6:$I$11,'Holgura'!$B$6:$B$11,$A80,'Holgura'!$E$6:$E$11,"Diego")+SUMIFS('Holgura'!$I$6:$I$11,'Holgura'!$B$6:$B$11,$A80,'Holgura'!$E$6:$E$11,"Ambos")+SUMIFS('Entrega'!$I$6:$I$9,'Entrega'!$B$6:$B$9,$A80,'Entrega'!$E$6:$E$9,"Diego")+SUMIFS('Entrega'!$I$6:$I$9,'Entrega'!$B$6:$B$9,$A80,'Entrega'!$E$6:$E$9,"Ambos")+SUMIFS('Defensa'!$I$6:$I$10,'Defensa'!$B$6:$B$10,$A80,'Defensa'!$E$6:$E$10,"Diego")+SUMIFS('Defensa'!$I$6:$I$10,'Defensa'!$B$6:$B$10,$A80,'Defensa'!$E$6:$E$10,"Ambos")</f>
+        <f>SUMIFS('S1'!$I$6:$I$32,'S1'!$B$6:$B$32,$A80,'S1'!$E$6:$E$32,"Diego")+SUMIFS('S1'!$I$6:$I$32,'S1'!$B$6:$B$32,$A80,'S1'!$E$6:$E$32,"Ambos")+SUMIFS('S2'!$I$6:$I$23,'S2'!$B$6:$B$23,$A80,'S2'!$E$6:$E$23,"Diego")+SUMIFS('S2'!$I$6:$I$23,'S2'!$B$6:$B$23,$A80,'S2'!$E$6:$E$23,"Ambos")+SUMIFS('S3'!$I$6:$I$24,'S3'!$B$6:$B$24,$A80,'S3'!$E$6:$E$24,"Diego")+SUMIFS('S3'!$I$6:$I$24,'S3'!$B$6:$B$24,$A80,'S3'!$E$6:$E$24,"Ambos")+SUMIFS('S4'!$I$6:$I$22,'S4'!$B$6:$B$22,$A80,'S4'!$E$6:$E$22,"Diego")+SUMIFS('S4'!$I$6:$I$22,'S4'!$B$6:$B$22,$A80,'S4'!$E$6:$E$22,"Ambos")+SUMIFS('S5'!$I$6:$I$20,'S5'!$B$6:$B$20,$A80,'S5'!$E$6:$E$20,"Diego")+SUMIFS('S5'!$I$6:$I$20,'S5'!$B$6:$B$20,$A80,'S5'!$E$6:$E$20,"Ambos")+SUMIFS('S6'!$I$6:$I$17,'S6'!$B$6:$B$17,$A80,'S6'!$E$6:$E$17,"Diego")+SUMIFS('S6'!$I$6:$I$17,'S6'!$B$6:$B$17,$A80,'S6'!$E$6:$E$17,"Ambos")+SUMIFS('S7'!$I$6:$I$19,'S7'!$B$6:$B$19,$A80,'S7'!$E$6:$E$19,"Diego")+SUMIFS('S7'!$I$6:$I$19,'S7'!$B$6:$B$19,$A80,'S7'!$E$6:$E$19,"Ambos")+SUMIFS('S8'!$I$6:$I$23,'S8'!$B$6:$B$23,$A80,'S8'!$E$6:$E$23,"Diego")+SUMIFS('S8'!$I$6:$I$23,'S8'!$B$6:$B$23,$A80,'S8'!$E$6:$E$23,"Ambos")+SUMIFS('S9'!$I$6:$I$15,'S9'!$B$6:$B$15,$A80,'S9'!$E$6:$E$15,"Diego")+SUMIFS('S9'!$I$6:$I$15,'S9'!$B$6:$B$15,$A80,'S9'!$E$6:$E$15,"Ambos")+SUMIFS('S10'!$I$6:$I$13,'S10'!$B$6:$B$13,$A80,'S10'!$E$6:$E$13,"Diego")+SUMIFS('S10'!$I$6:$I$13,'S10'!$B$6:$B$13,$A80,'S10'!$E$6:$E$13,"Ambos")+SUMIFS('Holgura'!$I$6:$I$11,'Holgura'!$B$6:$B$11,$A80,'Holgura'!$E$6:$E$11,"Diego")+SUMIFS('Holgura'!$I$6:$I$11,'Holgura'!$B$6:$B$11,$A80,'Holgura'!$E$6:$E$11,"Ambos")+SUMIFS('Entrega'!$I$6:$I$9,'Entrega'!$B$6:$B$9,$A80,'Entrega'!$E$6:$E$9,"Diego")+SUMIFS('Entrega'!$I$6:$I$9,'Entrega'!$B$6:$B$9,$A80,'Entrega'!$E$6:$E$9,"Ambos")+SUMIFS('Defensa'!$I$6:$I$10,'Defensa'!$B$6:$B$10,$A80,'Defensa'!$E$6:$E$10,"Diego")+SUMIFS('Defensa'!$I$6:$I$10,'Defensa'!$B$6:$B$10,$A80,'Defensa'!$E$6:$E$10,"Ambos")</f>
         <v/>
       </c>
       <c r="F80" s="21">
-        <f>COUNTIFS('S1'!$B$6:$B$32,$A80,'S1'!$E$6:$E$32,"Víctor")+COUNTIFS('S1'!$B$6:$B$32,$A80,'S1'!$E$6:$E$32,"Ambos")+COUNTIFS('S2'!$B$6:$B$23,$A80,'S2'!$E$6:$E$23,"Víctor")+COUNTIFS('S2'!$B$6:$B$23,$A80,'S2'!$E$6:$E$23,"Ambos")+COUNTIFS('S3'!$B$6:$B$19,$A80,'S3'!$E$6:$E$19,"Víctor")+COUNTIFS('S3'!$B$6:$B$19,$A80,'S3'!$E$6:$E$19,"Ambos")+COUNTIFS('S4'!$B$6:$B$20,$A80,'S4'!$E$6:$E$20,"Víctor")+COUNTIFS('S4'!$B$6:$B$20,$A80,'S4'!$E$6:$E$20,"Ambos")+COUNTIFS('S5'!$B$6:$B$20,$A80,'S5'!$E$6:$E$20,"Víctor")+COUNTIFS('S5'!$B$6:$B$20,$A80,'S5'!$E$6:$E$20,"Ambos")+COUNTIFS('S6'!$B$6:$B$17,$A80,'S6'!$E$6:$E$17,"Víctor")+COUNTIFS('S6'!$B$6:$B$17,$A80,'S6'!$E$6:$E$17,"Ambos")+COUNTIFS('S7'!$B$6:$B$19,$A80,'S7'!$E$6:$E$19,"Víctor")+COUNTIFS('S7'!$B$6:$B$19,$A80,'S7'!$E$6:$E$19,"Ambos")+COUNTIFS('S8'!$B$6:$B$23,$A80,'S8'!$E$6:$E$23,"Víctor")+COUNTIFS('S8'!$B$6:$B$23,$A80,'S8'!$E$6:$E$23,"Ambos")+COUNTIFS('S9'!$B$6:$B$15,$A80,'S9'!$E$6:$E$15,"Víctor")+COUNTIFS('S9'!$B$6:$B$15,$A80,'S9'!$E$6:$E$15,"Ambos")+COUNTIFS('S10'!$B$6:$B$13,$A80,'S10'!$E$6:$E$13,"Víctor")+COUNTIFS('S10'!$B$6:$B$13,$A80,'S10'!$E$6:$E$13,"Ambos")+COUNTIFS('Holgura'!$B$6:$B$11,$A80,'Holgura'!$E$6:$E$11,"Víctor")+COUNTIFS('Holgura'!$B$6:$B$11,$A80,'Holgura'!$E$6:$E$11,"Ambos")+COUNTIFS('Entrega'!$B$6:$B$9,$A80,'Entrega'!$E$6:$E$9,"Víctor")+COUNTIFS('Entrega'!$B$6:$B$9,$A80,'Entrega'!$E$6:$E$9,"Ambos")+COUNTIFS('Defensa'!$B$6:$B$10,$A80,'Defensa'!$E$6:$E$10,"Víctor")+COUNTIFS('Defensa'!$B$6:$B$10,$A80,'Defensa'!$E$6:$E$10,"Ambos")</f>
+        <f>COUNTIFS('S1'!$B$6:$B$32,$A80,'S1'!$E$6:$E$32,"Víctor")+COUNTIFS('S1'!$B$6:$B$32,$A80,'S1'!$E$6:$E$32,"Ambos")+COUNTIFS('S2'!$B$6:$B$23,$A80,'S2'!$E$6:$E$23,"Víctor")+COUNTIFS('S2'!$B$6:$B$23,$A80,'S2'!$E$6:$E$23,"Ambos")+COUNTIFS('S3'!$B$6:$B$24,$A80,'S3'!$E$6:$E$24,"Víctor")+COUNTIFS('S3'!$B$6:$B$24,$A80,'S3'!$E$6:$E$24,"Ambos")+COUNTIFS('S4'!$B$6:$B$22,$A80,'S4'!$E$6:$E$22,"Víctor")+COUNTIFS('S4'!$B$6:$B$22,$A80,'S4'!$E$6:$E$22,"Ambos")+COUNTIFS('S5'!$B$6:$B$20,$A80,'S5'!$E$6:$E$20,"Víctor")+COUNTIFS('S5'!$B$6:$B$20,$A80,'S5'!$E$6:$E$20,"Ambos")+COUNTIFS('S6'!$B$6:$B$17,$A80,'S6'!$E$6:$E$17,"Víctor")+COUNTIFS('S6'!$B$6:$B$17,$A80,'S6'!$E$6:$E$17,"Ambos")+COUNTIFS('S7'!$B$6:$B$19,$A80,'S7'!$E$6:$E$19,"Víctor")+COUNTIFS('S7'!$B$6:$B$19,$A80,'S7'!$E$6:$E$19,"Ambos")+COUNTIFS('S8'!$B$6:$B$23,$A80,'S8'!$E$6:$E$23,"Víctor")+COUNTIFS('S8'!$B$6:$B$23,$A80,'S8'!$E$6:$E$23,"Ambos")+COUNTIFS('S9'!$B$6:$B$15,$A80,'S9'!$E$6:$E$15,"Víctor")+COUNTIFS('S9'!$B$6:$B$15,$A80,'S9'!$E$6:$E$15,"Ambos")+COUNTIFS('S10'!$B$6:$B$13,$A80,'S10'!$E$6:$E$13,"Víctor")+COUNTIFS('S10'!$B$6:$B$13,$A80,'S10'!$E$6:$E$13,"Ambos")+COUNTIFS('Holgura'!$B$6:$B$11,$A80,'Holgura'!$E$6:$E$11,"Víctor")+COUNTIFS('Holgura'!$B$6:$B$11,$A80,'Holgura'!$E$6:$E$11,"Ambos")+COUNTIFS('Entrega'!$B$6:$B$9,$A80,'Entrega'!$E$6:$E$9,"Víctor")+COUNTIFS('Entrega'!$B$6:$B$9,$A80,'Entrega'!$E$6:$E$9,"Ambos")+COUNTIFS('Defensa'!$B$6:$B$10,$A80,'Defensa'!$E$6:$E$10,"Víctor")+COUNTIFS('Defensa'!$B$6:$B$10,$A80,'Defensa'!$E$6:$E$10,"Ambos")</f>
         <v/>
       </c>
       <c r="G80" s="21">
-        <f>COUNTIFS('S1'!$B$6:$B$32,$A80,'S1'!$E$6:$E$32,"Diego")+COUNTIFS('S1'!$B$6:$B$32,$A80,'S1'!$E$6:$E$32,"Ambos")+COUNTIFS('S2'!$B$6:$B$23,$A80,'S2'!$E$6:$E$23,"Diego")+COUNTIFS('S2'!$B$6:$B$23,$A80,'S2'!$E$6:$E$23,"Ambos")+COUNTIFS('S3'!$B$6:$B$19,$A80,'S3'!$E$6:$E$19,"Diego")+COUNTIFS('S3'!$B$6:$B$19,$A80,'S3'!$E$6:$E$19,"Ambos")+COUNTIFS('S4'!$B$6:$B$20,$A80,'S4'!$E$6:$E$20,"Diego")+COUNTIFS('S4'!$B$6:$B$20,$A80,'S4'!$E$6:$E$20,"Ambos")+COUNTIFS('S5'!$B$6:$B$20,$A80,'S5'!$E$6:$E$20,"Diego")+COUNTIFS('S5'!$B$6:$B$20,$A80,'S5'!$E$6:$E$20,"Ambos")+COUNTIFS('S6'!$B$6:$B$17,$A80,'S6'!$E$6:$E$17,"Diego")+COUNTIFS('S6'!$B$6:$B$17,$A80,'S6'!$E$6:$E$17,"Ambos")+COUNTIFS('S7'!$B$6:$B$19,$A80,'S7'!$E$6:$E$19,"Diego")+COUNTIFS('S7'!$B$6:$B$19,$A80,'S7'!$E$6:$E$19,"Ambos")+COUNTIFS('S8'!$B$6:$B$23,$A80,'S8'!$E$6:$E$23,"Diego")+COUNTIFS('S8'!$B$6:$B$23,$A80,'S8'!$E$6:$E$23,"Ambos")+COUNTIFS('S9'!$B$6:$B$15,$A80,'S9'!$E$6:$E$15,"Diego")+COUNTIFS('S9'!$B$6:$B$15,$A80,'S9'!$E$6:$E$15,"Ambos")+COUNTIFS('S10'!$B$6:$B$13,$A80,'S10'!$E$6:$E$13,"Diego")+COUNTIFS('S10'!$B$6:$B$13,$A80,'S10'!$E$6:$E$13,"Ambos")+COUNTIFS('Holgura'!$B$6:$B$11,$A80,'Holgura'!$E$6:$E$11,"Diego")+COUNTIFS('Holgura'!$B$6:$B$11,$A80,'Holgura'!$E$6:$E$11,"Ambos")+COUNTIFS('Entrega'!$B$6:$B$9,$A80,'Entrega'!$E$6:$E$9,"Diego")+COUNTIFS('Entrega'!$B$6:$B$9,$A80,'Entrega'!$E$6:$E$9,"Ambos")+COUNTIFS('Defensa'!$B$6:$B$10,$A80,'Defensa'!$E$6:$E$10,"Diego")+COUNTIFS('Defensa'!$B$6:$B$10,$A80,'Defensa'!$E$6:$E$10,"Ambos")</f>
+        <f>COUNTIFS('S1'!$B$6:$B$32,$A80,'S1'!$E$6:$E$32,"Diego")+COUNTIFS('S1'!$B$6:$B$32,$A80,'S1'!$E$6:$E$32,"Ambos")+COUNTIFS('S2'!$B$6:$B$23,$A80,'S2'!$E$6:$E$23,"Diego")+COUNTIFS('S2'!$B$6:$B$23,$A80,'S2'!$E$6:$E$23,"Ambos")+COUNTIFS('S3'!$B$6:$B$24,$A80,'S3'!$E$6:$E$24,"Diego")+COUNTIFS('S3'!$B$6:$B$24,$A80,'S3'!$E$6:$E$24,"Ambos")+COUNTIFS('S4'!$B$6:$B$22,$A80,'S4'!$E$6:$E$22,"Diego")+COUNTIFS('S4'!$B$6:$B$22,$A80,'S4'!$E$6:$E$22,"Ambos")+COUNTIFS('S5'!$B$6:$B$20,$A80,'S5'!$E$6:$E$20,"Diego")+COUNTIFS('S5'!$B$6:$B$20,$A80,'S5'!$E$6:$E$20,"Ambos")+COUNTIFS('S6'!$B$6:$B$17,$A80,'S6'!$E$6:$E$17,"Diego")+COUNTIFS('S6'!$B$6:$B$17,$A80,'S6'!$E$6:$E$17,"Ambos")+COUNTIFS('S7'!$B$6:$B$19,$A80,'S7'!$E$6:$E$19,"Diego")+COUNTIFS('S7'!$B$6:$B$19,$A80,'S7'!$E$6:$E$19,"Ambos")+COUNTIFS('S8'!$B$6:$B$23,$A80,'S8'!$E$6:$E$23,"Diego")+COUNTIFS('S8'!$B$6:$B$23,$A80,'S8'!$E$6:$E$23,"Ambos")+COUNTIFS('S9'!$B$6:$B$15,$A80,'S9'!$E$6:$E$15,"Diego")+COUNTIFS('S9'!$B$6:$B$15,$A80,'S9'!$E$6:$E$15,"Ambos")+COUNTIFS('S10'!$B$6:$B$13,$A80,'S10'!$E$6:$E$13,"Diego")+COUNTIFS('S10'!$B$6:$B$13,$A80,'S10'!$E$6:$E$13,"Ambos")+COUNTIFS('Holgura'!$B$6:$B$11,$A80,'Holgura'!$E$6:$E$11,"Diego")+COUNTIFS('Holgura'!$B$6:$B$11,$A80,'Holgura'!$E$6:$E$11,"Ambos")+COUNTIFS('Entrega'!$B$6:$B$9,$A80,'Entrega'!$E$6:$E$9,"Diego")+COUNTIFS('Entrega'!$B$6:$B$9,$A80,'Entrega'!$E$6:$E$9,"Ambos")+COUNTIFS('Defensa'!$B$6:$B$10,$A80,'Defensa'!$E$6:$E$10,"Diego")+COUNTIFS('Defensa'!$B$6:$B$10,$A80,'Defensa'!$E$6:$E$10,"Ambos")</f>
         <v/>
       </c>
     </row>
@@ -10884,19 +10905,19 @@
         <v/>
       </c>
       <c r="D81" s="21">
-        <f>SUMIFS('S1'!$I$6:$I$32,'S1'!$B$6:$B$32,$A81,'S1'!$E$6:$E$32,"Víctor")+SUMIFS('S1'!$I$6:$I$32,'S1'!$B$6:$B$32,$A81,'S1'!$E$6:$E$32,"Ambos")+SUMIFS('S2'!$I$6:$I$23,'S2'!$B$6:$B$23,$A81,'S2'!$E$6:$E$23,"Víctor")+SUMIFS('S2'!$I$6:$I$23,'S2'!$B$6:$B$23,$A81,'S2'!$E$6:$E$23,"Ambos")+SUMIFS('S3'!$I$6:$I$19,'S3'!$B$6:$B$19,$A81,'S3'!$E$6:$E$19,"Víctor")+SUMIFS('S3'!$I$6:$I$19,'S3'!$B$6:$B$19,$A81,'S3'!$E$6:$E$19,"Ambos")+SUMIFS('S4'!$I$6:$I$20,'S4'!$B$6:$B$20,$A81,'S4'!$E$6:$E$20,"Víctor")+SUMIFS('S4'!$I$6:$I$20,'S4'!$B$6:$B$20,$A81,'S4'!$E$6:$E$20,"Ambos")+SUMIFS('S5'!$I$6:$I$20,'S5'!$B$6:$B$20,$A81,'S5'!$E$6:$E$20,"Víctor")+SUMIFS('S5'!$I$6:$I$20,'S5'!$B$6:$B$20,$A81,'S5'!$E$6:$E$20,"Ambos")+SUMIFS('S6'!$I$6:$I$17,'S6'!$B$6:$B$17,$A81,'S6'!$E$6:$E$17,"Víctor")+SUMIFS('S6'!$I$6:$I$17,'S6'!$B$6:$B$17,$A81,'S6'!$E$6:$E$17,"Ambos")+SUMIFS('S7'!$I$6:$I$19,'S7'!$B$6:$B$19,$A81,'S7'!$E$6:$E$19,"Víctor")+SUMIFS('S7'!$I$6:$I$19,'S7'!$B$6:$B$19,$A81,'S7'!$E$6:$E$19,"Ambos")+SUMIFS('S8'!$I$6:$I$23,'S8'!$B$6:$B$23,$A81,'S8'!$E$6:$E$23,"Víctor")+SUMIFS('S8'!$I$6:$I$23,'S8'!$B$6:$B$23,$A81,'S8'!$E$6:$E$23,"Ambos")+SUMIFS('S9'!$I$6:$I$15,'S9'!$B$6:$B$15,$A81,'S9'!$E$6:$E$15,"Víctor")+SUMIFS('S9'!$I$6:$I$15,'S9'!$B$6:$B$15,$A81,'S9'!$E$6:$E$15,"Ambos")+SUMIFS('S10'!$I$6:$I$13,'S10'!$B$6:$B$13,$A81,'S10'!$E$6:$E$13,"Víctor")+SUMIFS('S10'!$I$6:$I$13,'S10'!$B$6:$B$13,$A81,'S10'!$E$6:$E$13,"Ambos")+SUMIFS('Holgura'!$I$6:$I$11,'Holgura'!$B$6:$B$11,$A81,'Holgura'!$E$6:$E$11,"Víctor")+SUMIFS('Holgura'!$I$6:$I$11,'Holgura'!$B$6:$B$11,$A81,'Holgura'!$E$6:$E$11,"Ambos")+SUMIFS('Entrega'!$I$6:$I$9,'Entrega'!$B$6:$B$9,$A81,'Entrega'!$E$6:$E$9,"Víctor")+SUMIFS('Entrega'!$I$6:$I$9,'Entrega'!$B$6:$B$9,$A81,'Entrega'!$E$6:$E$9,"Ambos")+SUMIFS('Defensa'!$I$6:$I$10,'Defensa'!$B$6:$B$10,$A81,'Defensa'!$E$6:$E$10,"Víctor")+SUMIFS('Defensa'!$I$6:$I$10,'Defensa'!$B$6:$B$10,$A81,'Defensa'!$E$6:$E$10,"Ambos")</f>
+        <f>SUMIFS('S1'!$I$6:$I$32,'S1'!$B$6:$B$32,$A81,'S1'!$E$6:$E$32,"Víctor")+SUMIFS('S1'!$I$6:$I$32,'S1'!$B$6:$B$32,$A81,'S1'!$E$6:$E$32,"Ambos")+SUMIFS('S2'!$I$6:$I$23,'S2'!$B$6:$B$23,$A81,'S2'!$E$6:$E$23,"Víctor")+SUMIFS('S2'!$I$6:$I$23,'S2'!$B$6:$B$23,$A81,'S2'!$E$6:$E$23,"Ambos")+SUMIFS('S3'!$I$6:$I$24,'S3'!$B$6:$B$24,$A81,'S3'!$E$6:$E$24,"Víctor")+SUMIFS('S3'!$I$6:$I$24,'S3'!$B$6:$B$24,$A81,'S3'!$E$6:$E$24,"Ambos")+SUMIFS('S4'!$I$6:$I$22,'S4'!$B$6:$B$22,$A81,'S4'!$E$6:$E$22,"Víctor")+SUMIFS('S4'!$I$6:$I$22,'S4'!$B$6:$B$22,$A81,'S4'!$E$6:$E$22,"Ambos")+SUMIFS('S5'!$I$6:$I$20,'S5'!$B$6:$B$20,$A81,'S5'!$E$6:$E$20,"Víctor")+SUMIFS('S5'!$I$6:$I$20,'S5'!$B$6:$B$20,$A81,'S5'!$E$6:$E$20,"Ambos")+SUMIFS('S6'!$I$6:$I$17,'S6'!$B$6:$B$17,$A81,'S6'!$E$6:$E$17,"Víctor")+SUMIFS('S6'!$I$6:$I$17,'S6'!$B$6:$B$17,$A81,'S6'!$E$6:$E$17,"Ambos")+SUMIFS('S7'!$I$6:$I$19,'S7'!$B$6:$B$19,$A81,'S7'!$E$6:$E$19,"Víctor")+SUMIFS('S7'!$I$6:$I$19,'S7'!$B$6:$B$19,$A81,'S7'!$E$6:$E$19,"Ambos")+SUMIFS('S8'!$I$6:$I$23,'S8'!$B$6:$B$23,$A81,'S8'!$E$6:$E$23,"Víctor")+SUMIFS('S8'!$I$6:$I$23,'S8'!$B$6:$B$23,$A81,'S8'!$E$6:$E$23,"Ambos")+SUMIFS('S9'!$I$6:$I$15,'S9'!$B$6:$B$15,$A81,'S9'!$E$6:$E$15,"Víctor")+SUMIFS('S9'!$I$6:$I$15,'S9'!$B$6:$B$15,$A81,'S9'!$E$6:$E$15,"Ambos")+SUMIFS('S10'!$I$6:$I$13,'S10'!$B$6:$B$13,$A81,'S10'!$E$6:$E$13,"Víctor")+SUMIFS('S10'!$I$6:$I$13,'S10'!$B$6:$B$13,$A81,'S10'!$E$6:$E$13,"Ambos")+SUMIFS('Holgura'!$I$6:$I$11,'Holgura'!$B$6:$B$11,$A81,'Holgura'!$E$6:$E$11,"Víctor")+SUMIFS('Holgura'!$I$6:$I$11,'Holgura'!$B$6:$B$11,$A81,'Holgura'!$E$6:$E$11,"Ambos")+SUMIFS('Entrega'!$I$6:$I$9,'Entrega'!$B$6:$B$9,$A81,'Entrega'!$E$6:$E$9,"Víctor")+SUMIFS('Entrega'!$I$6:$I$9,'Entrega'!$B$6:$B$9,$A81,'Entrega'!$E$6:$E$9,"Ambos")+SUMIFS('Defensa'!$I$6:$I$10,'Defensa'!$B$6:$B$10,$A81,'Defensa'!$E$6:$E$10,"Víctor")+SUMIFS('Defensa'!$I$6:$I$10,'Defensa'!$B$6:$B$10,$A81,'Defensa'!$E$6:$E$10,"Ambos")</f>
         <v/>
       </c>
       <c r="E81" s="21">
-        <f>SUMIFS('S1'!$I$6:$I$32,'S1'!$B$6:$B$32,$A81,'S1'!$E$6:$E$32,"Diego")+SUMIFS('S1'!$I$6:$I$32,'S1'!$B$6:$B$32,$A81,'S1'!$E$6:$E$32,"Ambos")+SUMIFS('S2'!$I$6:$I$23,'S2'!$B$6:$B$23,$A81,'S2'!$E$6:$E$23,"Diego")+SUMIFS('S2'!$I$6:$I$23,'S2'!$B$6:$B$23,$A81,'S2'!$E$6:$E$23,"Ambos")+SUMIFS('S3'!$I$6:$I$19,'S3'!$B$6:$B$19,$A81,'S3'!$E$6:$E$19,"Diego")+SUMIFS('S3'!$I$6:$I$19,'S3'!$B$6:$B$19,$A81,'S3'!$E$6:$E$19,"Ambos")+SUMIFS('S4'!$I$6:$I$20,'S4'!$B$6:$B$20,$A81,'S4'!$E$6:$E$20,"Diego")+SUMIFS('S4'!$I$6:$I$20,'S4'!$B$6:$B$20,$A81,'S4'!$E$6:$E$20,"Ambos")+SUMIFS('S5'!$I$6:$I$20,'S5'!$B$6:$B$20,$A81,'S5'!$E$6:$E$20,"Diego")+SUMIFS('S5'!$I$6:$I$20,'S5'!$B$6:$B$20,$A81,'S5'!$E$6:$E$20,"Ambos")+SUMIFS('S6'!$I$6:$I$17,'S6'!$B$6:$B$17,$A81,'S6'!$E$6:$E$17,"Diego")+SUMIFS('S6'!$I$6:$I$17,'S6'!$B$6:$B$17,$A81,'S6'!$E$6:$E$17,"Ambos")+SUMIFS('S7'!$I$6:$I$19,'S7'!$B$6:$B$19,$A81,'S7'!$E$6:$E$19,"Diego")+SUMIFS('S7'!$I$6:$I$19,'S7'!$B$6:$B$19,$A81,'S7'!$E$6:$E$19,"Ambos")+SUMIFS('S8'!$I$6:$I$23,'S8'!$B$6:$B$23,$A81,'S8'!$E$6:$E$23,"Diego")+SUMIFS('S8'!$I$6:$I$23,'S8'!$B$6:$B$23,$A81,'S8'!$E$6:$E$23,"Ambos")+SUMIFS('S9'!$I$6:$I$15,'S9'!$B$6:$B$15,$A81,'S9'!$E$6:$E$15,"Diego")+SUMIFS('S9'!$I$6:$I$15,'S9'!$B$6:$B$15,$A81,'S9'!$E$6:$E$15,"Ambos")+SUMIFS('S10'!$I$6:$I$13,'S10'!$B$6:$B$13,$A81,'S10'!$E$6:$E$13,"Diego")+SUMIFS('S10'!$I$6:$I$13,'S10'!$B$6:$B$13,$A81,'S10'!$E$6:$E$13,"Ambos")+SUMIFS('Holgura'!$I$6:$I$11,'Holgura'!$B$6:$B$11,$A81,'Holgura'!$E$6:$E$11,"Diego")+SUMIFS('Holgura'!$I$6:$I$11,'Holgura'!$B$6:$B$11,$A81,'Holgura'!$E$6:$E$11,"Ambos")+SUMIFS('Entrega'!$I$6:$I$9,'Entrega'!$B$6:$B$9,$A81,'Entrega'!$E$6:$E$9,"Diego")+SUMIFS('Entrega'!$I$6:$I$9,'Entrega'!$B$6:$B$9,$A81,'Entrega'!$E$6:$E$9,"Ambos")+SUMIFS('Defensa'!$I$6:$I$10,'Defensa'!$B$6:$B$10,$A81,'Defensa'!$E$6:$E$10,"Diego")+SUMIFS('Defensa'!$I$6:$I$10,'Defensa'!$B$6:$B$10,$A81,'Defensa'!$E$6:$E$10,"Ambos")</f>
+        <f>SUMIFS('S1'!$I$6:$I$32,'S1'!$B$6:$B$32,$A81,'S1'!$E$6:$E$32,"Diego")+SUMIFS('S1'!$I$6:$I$32,'S1'!$B$6:$B$32,$A81,'S1'!$E$6:$E$32,"Ambos")+SUMIFS('S2'!$I$6:$I$23,'S2'!$B$6:$B$23,$A81,'S2'!$E$6:$E$23,"Diego")+SUMIFS('S2'!$I$6:$I$23,'S2'!$B$6:$B$23,$A81,'S2'!$E$6:$E$23,"Ambos")+SUMIFS('S3'!$I$6:$I$24,'S3'!$B$6:$B$24,$A81,'S3'!$E$6:$E$24,"Diego")+SUMIFS('S3'!$I$6:$I$24,'S3'!$B$6:$B$24,$A81,'S3'!$E$6:$E$24,"Ambos")+SUMIFS('S4'!$I$6:$I$22,'S4'!$B$6:$B$22,$A81,'S4'!$E$6:$E$22,"Diego")+SUMIFS('S4'!$I$6:$I$22,'S4'!$B$6:$B$22,$A81,'S4'!$E$6:$E$22,"Ambos")+SUMIFS('S5'!$I$6:$I$20,'S5'!$B$6:$B$20,$A81,'S5'!$E$6:$E$20,"Diego")+SUMIFS('S5'!$I$6:$I$20,'S5'!$B$6:$B$20,$A81,'S5'!$E$6:$E$20,"Ambos")+SUMIFS('S6'!$I$6:$I$17,'S6'!$B$6:$B$17,$A81,'S6'!$E$6:$E$17,"Diego")+SUMIFS('S6'!$I$6:$I$17,'S6'!$B$6:$B$17,$A81,'S6'!$E$6:$E$17,"Ambos")+SUMIFS('S7'!$I$6:$I$19,'S7'!$B$6:$B$19,$A81,'S7'!$E$6:$E$19,"Diego")+SUMIFS('S7'!$I$6:$I$19,'S7'!$B$6:$B$19,$A81,'S7'!$E$6:$E$19,"Ambos")+SUMIFS('S8'!$I$6:$I$23,'S8'!$B$6:$B$23,$A81,'S8'!$E$6:$E$23,"Diego")+SUMIFS('S8'!$I$6:$I$23,'S8'!$B$6:$B$23,$A81,'S8'!$E$6:$E$23,"Ambos")+SUMIFS('S9'!$I$6:$I$15,'S9'!$B$6:$B$15,$A81,'S9'!$E$6:$E$15,"Diego")+SUMIFS('S9'!$I$6:$I$15,'S9'!$B$6:$B$15,$A81,'S9'!$E$6:$E$15,"Ambos")+SUMIFS('S10'!$I$6:$I$13,'S10'!$B$6:$B$13,$A81,'S10'!$E$6:$E$13,"Diego")+SUMIFS('S10'!$I$6:$I$13,'S10'!$B$6:$B$13,$A81,'S10'!$E$6:$E$13,"Ambos")+SUMIFS('Holgura'!$I$6:$I$11,'Holgura'!$B$6:$B$11,$A81,'Holgura'!$E$6:$E$11,"Diego")+SUMIFS('Holgura'!$I$6:$I$11,'Holgura'!$B$6:$B$11,$A81,'Holgura'!$E$6:$E$11,"Ambos")+SUMIFS('Entrega'!$I$6:$I$9,'Entrega'!$B$6:$B$9,$A81,'Entrega'!$E$6:$E$9,"Diego")+SUMIFS('Entrega'!$I$6:$I$9,'Entrega'!$B$6:$B$9,$A81,'Entrega'!$E$6:$E$9,"Ambos")+SUMIFS('Defensa'!$I$6:$I$10,'Defensa'!$B$6:$B$10,$A81,'Defensa'!$E$6:$E$10,"Diego")+SUMIFS('Defensa'!$I$6:$I$10,'Defensa'!$B$6:$B$10,$A81,'Defensa'!$E$6:$E$10,"Ambos")</f>
         <v/>
       </c>
       <c r="F81" s="21">
-        <f>COUNTIFS('S1'!$B$6:$B$32,$A81,'S1'!$E$6:$E$32,"Víctor")+COUNTIFS('S1'!$B$6:$B$32,$A81,'S1'!$E$6:$E$32,"Ambos")+COUNTIFS('S2'!$B$6:$B$23,$A81,'S2'!$E$6:$E$23,"Víctor")+COUNTIFS('S2'!$B$6:$B$23,$A81,'S2'!$E$6:$E$23,"Ambos")+COUNTIFS('S3'!$B$6:$B$19,$A81,'S3'!$E$6:$E$19,"Víctor")+COUNTIFS('S3'!$B$6:$B$19,$A81,'S3'!$E$6:$E$19,"Ambos")+COUNTIFS('S4'!$B$6:$B$20,$A81,'S4'!$E$6:$E$20,"Víctor")+COUNTIFS('S4'!$B$6:$B$20,$A81,'S4'!$E$6:$E$20,"Ambos")+COUNTIFS('S5'!$B$6:$B$20,$A81,'S5'!$E$6:$E$20,"Víctor")+COUNTIFS('S5'!$B$6:$B$20,$A81,'S5'!$E$6:$E$20,"Ambos")+COUNTIFS('S6'!$B$6:$B$17,$A81,'S6'!$E$6:$E$17,"Víctor")+COUNTIFS('S6'!$B$6:$B$17,$A81,'S6'!$E$6:$E$17,"Ambos")+COUNTIFS('S7'!$B$6:$B$19,$A81,'S7'!$E$6:$E$19,"Víctor")+COUNTIFS('S7'!$B$6:$B$19,$A81,'S7'!$E$6:$E$19,"Ambos")+COUNTIFS('S8'!$B$6:$B$23,$A81,'S8'!$E$6:$E$23,"Víctor")+COUNTIFS('S8'!$B$6:$B$23,$A81,'S8'!$E$6:$E$23,"Ambos")+COUNTIFS('S9'!$B$6:$B$15,$A81,'S9'!$E$6:$E$15,"Víctor")+COUNTIFS('S9'!$B$6:$B$15,$A81,'S9'!$E$6:$E$15,"Ambos")+COUNTIFS('S10'!$B$6:$B$13,$A81,'S10'!$E$6:$E$13,"Víctor")+COUNTIFS('S10'!$B$6:$B$13,$A81,'S10'!$E$6:$E$13,"Ambos")+COUNTIFS('Holgura'!$B$6:$B$11,$A81,'Holgura'!$E$6:$E$11,"Víctor")+COUNTIFS('Holgura'!$B$6:$B$11,$A81,'Holgura'!$E$6:$E$11,"Ambos")+COUNTIFS('Entrega'!$B$6:$B$9,$A81,'Entrega'!$E$6:$E$9,"Víctor")+COUNTIFS('Entrega'!$B$6:$B$9,$A81,'Entrega'!$E$6:$E$9,"Ambos")+COUNTIFS('Defensa'!$B$6:$B$10,$A81,'Defensa'!$E$6:$E$10,"Víctor")+COUNTIFS('Defensa'!$B$6:$B$10,$A81,'Defensa'!$E$6:$E$10,"Ambos")</f>
+        <f>COUNTIFS('S1'!$B$6:$B$32,$A81,'S1'!$E$6:$E$32,"Víctor")+COUNTIFS('S1'!$B$6:$B$32,$A81,'S1'!$E$6:$E$32,"Ambos")+COUNTIFS('S2'!$B$6:$B$23,$A81,'S2'!$E$6:$E$23,"Víctor")+COUNTIFS('S2'!$B$6:$B$23,$A81,'S2'!$E$6:$E$23,"Ambos")+COUNTIFS('S3'!$B$6:$B$24,$A81,'S3'!$E$6:$E$24,"Víctor")+COUNTIFS('S3'!$B$6:$B$24,$A81,'S3'!$E$6:$E$24,"Ambos")+COUNTIFS('S4'!$B$6:$B$22,$A81,'S4'!$E$6:$E$22,"Víctor")+COUNTIFS('S4'!$B$6:$B$22,$A81,'S4'!$E$6:$E$22,"Ambos")+COUNTIFS('S5'!$B$6:$B$20,$A81,'S5'!$E$6:$E$20,"Víctor")+COUNTIFS('S5'!$B$6:$B$20,$A81,'S5'!$E$6:$E$20,"Ambos")+COUNTIFS('S6'!$B$6:$B$17,$A81,'S6'!$E$6:$E$17,"Víctor")+COUNTIFS('S6'!$B$6:$B$17,$A81,'S6'!$E$6:$E$17,"Ambos")+COUNTIFS('S7'!$B$6:$B$19,$A81,'S7'!$E$6:$E$19,"Víctor")+COUNTIFS('S7'!$B$6:$B$19,$A81,'S7'!$E$6:$E$19,"Ambos")+COUNTIFS('S8'!$B$6:$B$23,$A81,'S8'!$E$6:$E$23,"Víctor")+COUNTIFS('S8'!$B$6:$B$23,$A81,'S8'!$E$6:$E$23,"Ambos")+COUNTIFS('S9'!$B$6:$B$15,$A81,'S9'!$E$6:$E$15,"Víctor")+COUNTIFS('S9'!$B$6:$B$15,$A81,'S9'!$E$6:$E$15,"Ambos")+COUNTIFS('S10'!$B$6:$B$13,$A81,'S10'!$E$6:$E$13,"Víctor")+COUNTIFS('S10'!$B$6:$B$13,$A81,'S10'!$E$6:$E$13,"Ambos")+COUNTIFS('Holgura'!$B$6:$B$11,$A81,'Holgura'!$E$6:$E$11,"Víctor")+COUNTIFS('Holgura'!$B$6:$B$11,$A81,'Holgura'!$E$6:$E$11,"Ambos")+COUNTIFS('Entrega'!$B$6:$B$9,$A81,'Entrega'!$E$6:$E$9,"Víctor")+COUNTIFS('Entrega'!$B$6:$B$9,$A81,'Entrega'!$E$6:$E$9,"Ambos")+COUNTIFS('Defensa'!$B$6:$B$10,$A81,'Defensa'!$E$6:$E$10,"Víctor")+COUNTIFS('Defensa'!$B$6:$B$10,$A81,'Defensa'!$E$6:$E$10,"Ambos")</f>
         <v/>
       </c>
       <c r="G81" s="21">
-        <f>COUNTIFS('S1'!$B$6:$B$32,$A81,'S1'!$E$6:$E$32,"Diego")+COUNTIFS('S1'!$B$6:$B$32,$A81,'S1'!$E$6:$E$32,"Ambos")+COUNTIFS('S2'!$B$6:$B$23,$A81,'S2'!$E$6:$E$23,"Diego")+COUNTIFS('S2'!$B$6:$B$23,$A81,'S2'!$E$6:$E$23,"Ambos")+COUNTIFS('S3'!$B$6:$B$19,$A81,'S3'!$E$6:$E$19,"Diego")+COUNTIFS('S3'!$B$6:$B$19,$A81,'S3'!$E$6:$E$19,"Ambos")+COUNTIFS('S4'!$B$6:$B$20,$A81,'S4'!$E$6:$E$20,"Diego")+COUNTIFS('S4'!$B$6:$B$20,$A81,'S4'!$E$6:$E$20,"Ambos")+COUNTIFS('S5'!$B$6:$B$20,$A81,'S5'!$E$6:$E$20,"Diego")+COUNTIFS('S5'!$B$6:$B$20,$A81,'S5'!$E$6:$E$20,"Ambos")+COUNTIFS('S6'!$B$6:$B$17,$A81,'S6'!$E$6:$E$17,"Diego")+COUNTIFS('S6'!$B$6:$B$17,$A81,'S6'!$E$6:$E$17,"Ambos")+COUNTIFS('S7'!$B$6:$B$19,$A81,'S7'!$E$6:$E$19,"Diego")+COUNTIFS('S7'!$B$6:$B$19,$A81,'S7'!$E$6:$E$19,"Ambos")+COUNTIFS('S8'!$B$6:$B$23,$A81,'S8'!$E$6:$E$23,"Diego")+COUNTIFS('S8'!$B$6:$B$23,$A81,'S8'!$E$6:$E$23,"Ambos")+COUNTIFS('S9'!$B$6:$B$15,$A81,'S9'!$E$6:$E$15,"Diego")+COUNTIFS('S9'!$B$6:$B$15,$A81,'S9'!$E$6:$E$15,"Ambos")+COUNTIFS('S10'!$B$6:$B$13,$A81,'S10'!$E$6:$E$13,"Diego")+COUNTIFS('S10'!$B$6:$B$13,$A81,'S10'!$E$6:$E$13,"Ambos")+COUNTIFS('Holgura'!$B$6:$B$11,$A81,'Holgura'!$E$6:$E$11,"Diego")+COUNTIFS('Holgura'!$B$6:$B$11,$A81,'Holgura'!$E$6:$E$11,"Ambos")+COUNTIFS('Entrega'!$B$6:$B$9,$A81,'Entrega'!$E$6:$E$9,"Diego")+COUNTIFS('Entrega'!$B$6:$B$9,$A81,'Entrega'!$E$6:$E$9,"Ambos")+COUNTIFS('Defensa'!$B$6:$B$10,$A81,'Defensa'!$E$6:$E$10,"Diego")+COUNTIFS('Defensa'!$B$6:$B$10,$A81,'Defensa'!$E$6:$E$10,"Ambos")</f>
+        <f>COUNTIFS('S1'!$B$6:$B$32,$A81,'S1'!$E$6:$E$32,"Diego")+COUNTIFS('S1'!$B$6:$B$32,$A81,'S1'!$E$6:$E$32,"Ambos")+COUNTIFS('S2'!$B$6:$B$23,$A81,'S2'!$E$6:$E$23,"Diego")+COUNTIFS('S2'!$B$6:$B$23,$A81,'S2'!$E$6:$E$23,"Ambos")+COUNTIFS('S3'!$B$6:$B$24,$A81,'S3'!$E$6:$E$24,"Diego")+COUNTIFS('S3'!$B$6:$B$24,$A81,'S3'!$E$6:$E$24,"Ambos")+COUNTIFS('S4'!$B$6:$B$22,$A81,'S4'!$E$6:$E$22,"Diego")+COUNTIFS('S4'!$B$6:$B$22,$A81,'S4'!$E$6:$E$22,"Ambos")+COUNTIFS('S5'!$B$6:$B$20,$A81,'S5'!$E$6:$E$20,"Diego")+COUNTIFS('S5'!$B$6:$B$20,$A81,'S5'!$E$6:$E$20,"Ambos")+COUNTIFS('S6'!$B$6:$B$17,$A81,'S6'!$E$6:$E$17,"Diego")+COUNTIFS('S6'!$B$6:$B$17,$A81,'S6'!$E$6:$E$17,"Ambos")+COUNTIFS('S7'!$B$6:$B$19,$A81,'S7'!$E$6:$E$19,"Diego")+COUNTIFS('S7'!$B$6:$B$19,$A81,'S7'!$E$6:$E$19,"Ambos")+COUNTIFS('S8'!$B$6:$B$23,$A81,'S8'!$E$6:$E$23,"Diego")+COUNTIFS('S8'!$B$6:$B$23,$A81,'S8'!$E$6:$E$23,"Ambos")+COUNTIFS('S9'!$B$6:$B$15,$A81,'S9'!$E$6:$E$15,"Diego")+COUNTIFS('S9'!$B$6:$B$15,$A81,'S9'!$E$6:$E$15,"Ambos")+COUNTIFS('S10'!$B$6:$B$13,$A81,'S10'!$E$6:$E$13,"Diego")+COUNTIFS('S10'!$B$6:$B$13,$A81,'S10'!$E$6:$E$13,"Ambos")+COUNTIFS('Holgura'!$B$6:$B$11,$A81,'Holgura'!$E$6:$E$11,"Diego")+COUNTIFS('Holgura'!$B$6:$B$11,$A81,'Holgura'!$E$6:$E$11,"Ambos")+COUNTIFS('Entrega'!$B$6:$B$9,$A81,'Entrega'!$E$6:$E$9,"Diego")+COUNTIFS('Entrega'!$B$6:$B$9,$A81,'Entrega'!$E$6:$E$9,"Ambos")+COUNTIFS('Defensa'!$B$6:$B$10,$A81,'Defensa'!$E$6:$E$10,"Diego")+COUNTIFS('Defensa'!$B$6:$B$10,$A81,'Defensa'!$E$6:$E$10,"Ambos")</f>
         <v/>
       </c>
     </row>
@@ -10913,19 +10934,19 @@
         <v/>
       </c>
       <c r="D82" s="21">
-        <f>SUMIFS('S1'!$I$6:$I$32,'S1'!$B$6:$B$32,$A82,'S1'!$E$6:$E$32,"Víctor")+SUMIFS('S1'!$I$6:$I$32,'S1'!$B$6:$B$32,$A82,'S1'!$E$6:$E$32,"Ambos")+SUMIFS('S2'!$I$6:$I$23,'S2'!$B$6:$B$23,$A82,'S2'!$E$6:$E$23,"Víctor")+SUMIFS('S2'!$I$6:$I$23,'S2'!$B$6:$B$23,$A82,'S2'!$E$6:$E$23,"Ambos")+SUMIFS('S3'!$I$6:$I$19,'S3'!$B$6:$B$19,$A82,'S3'!$E$6:$E$19,"Víctor")+SUMIFS('S3'!$I$6:$I$19,'S3'!$B$6:$B$19,$A82,'S3'!$E$6:$E$19,"Ambos")+SUMIFS('S4'!$I$6:$I$20,'S4'!$B$6:$B$20,$A82,'S4'!$E$6:$E$20,"Víctor")+SUMIFS('S4'!$I$6:$I$20,'S4'!$B$6:$B$20,$A82,'S4'!$E$6:$E$20,"Ambos")+SUMIFS('S5'!$I$6:$I$20,'S5'!$B$6:$B$20,$A82,'S5'!$E$6:$E$20,"Víctor")+SUMIFS('S5'!$I$6:$I$20,'S5'!$B$6:$B$20,$A82,'S5'!$E$6:$E$20,"Ambos")+SUMIFS('S6'!$I$6:$I$17,'S6'!$B$6:$B$17,$A82,'S6'!$E$6:$E$17,"Víctor")+SUMIFS('S6'!$I$6:$I$17,'S6'!$B$6:$B$17,$A82,'S6'!$E$6:$E$17,"Ambos")+SUMIFS('S7'!$I$6:$I$19,'S7'!$B$6:$B$19,$A82,'S7'!$E$6:$E$19,"Víctor")+SUMIFS('S7'!$I$6:$I$19,'S7'!$B$6:$B$19,$A82,'S7'!$E$6:$E$19,"Ambos")+SUMIFS('S8'!$I$6:$I$23,'S8'!$B$6:$B$23,$A82,'S8'!$E$6:$E$23,"Víctor")+SUMIFS('S8'!$I$6:$I$23,'S8'!$B$6:$B$23,$A82,'S8'!$E$6:$E$23,"Ambos")+SUMIFS('S9'!$I$6:$I$15,'S9'!$B$6:$B$15,$A82,'S9'!$E$6:$E$15,"Víctor")+SUMIFS('S9'!$I$6:$I$15,'S9'!$B$6:$B$15,$A82,'S9'!$E$6:$E$15,"Ambos")+SUMIFS('S10'!$I$6:$I$13,'S10'!$B$6:$B$13,$A82,'S10'!$E$6:$E$13,"Víctor")+SUMIFS('S10'!$I$6:$I$13,'S10'!$B$6:$B$13,$A82,'S10'!$E$6:$E$13,"Ambos")+SUMIFS('Holgura'!$I$6:$I$11,'Holgura'!$B$6:$B$11,$A82,'Holgura'!$E$6:$E$11,"Víctor")+SUMIFS('Holgura'!$I$6:$I$11,'Holgura'!$B$6:$B$11,$A82,'Holgura'!$E$6:$E$11,"Ambos")+SUMIFS('Entrega'!$I$6:$I$9,'Entrega'!$B$6:$B$9,$A82,'Entrega'!$E$6:$E$9,"Víctor")+SUMIFS('Entrega'!$I$6:$I$9,'Entrega'!$B$6:$B$9,$A82,'Entrega'!$E$6:$E$9,"Ambos")+SUMIFS('Defensa'!$I$6:$I$10,'Defensa'!$B$6:$B$10,$A82,'Defensa'!$E$6:$E$10,"Víctor")+SUMIFS('Defensa'!$I$6:$I$10,'Defensa'!$B$6:$B$10,$A82,'Defensa'!$E$6:$E$10,"Ambos")</f>
+        <f>SUMIFS('S1'!$I$6:$I$32,'S1'!$B$6:$B$32,$A82,'S1'!$E$6:$E$32,"Víctor")+SUMIFS('S1'!$I$6:$I$32,'S1'!$B$6:$B$32,$A82,'S1'!$E$6:$E$32,"Ambos")+SUMIFS('S2'!$I$6:$I$23,'S2'!$B$6:$B$23,$A82,'S2'!$E$6:$E$23,"Víctor")+SUMIFS('S2'!$I$6:$I$23,'S2'!$B$6:$B$23,$A82,'S2'!$E$6:$E$23,"Ambos")+SUMIFS('S3'!$I$6:$I$24,'S3'!$B$6:$B$24,$A82,'S3'!$E$6:$E$24,"Víctor")+SUMIFS('S3'!$I$6:$I$24,'S3'!$B$6:$B$24,$A82,'S3'!$E$6:$E$24,"Ambos")+SUMIFS('S4'!$I$6:$I$22,'S4'!$B$6:$B$22,$A82,'S4'!$E$6:$E$22,"Víctor")+SUMIFS('S4'!$I$6:$I$22,'S4'!$B$6:$B$22,$A82,'S4'!$E$6:$E$22,"Ambos")+SUMIFS('S5'!$I$6:$I$20,'S5'!$B$6:$B$20,$A82,'S5'!$E$6:$E$20,"Víctor")+SUMIFS('S5'!$I$6:$I$20,'S5'!$B$6:$B$20,$A82,'S5'!$E$6:$E$20,"Ambos")+SUMIFS('S6'!$I$6:$I$17,'S6'!$B$6:$B$17,$A82,'S6'!$E$6:$E$17,"Víctor")+SUMIFS('S6'!$I$6:$I$17,'S6'!$B$6:$B$17,$A82,'S6'!$E$6:$E$17,"Ambos")+SUMIFS('S7'!$I$6:$I$19,'S7'!$B$6:$B$19,$A82,'S7'!$E$6:$E$19,"Víctor")+SUMIFS('S7'!$I$6:$I$19,'S7'!$B$6:$B$19,$A82,'S7'!$E$6:$E$19,"Ambos")+SUMIFS('S8'!$I$6:$I$23,'S8'!$B$6:$B$23,$A82,'S8'!$E$6:$E$23,"Víctor")+SUMIFS('S8'!$I$6:$I$23,'S8'!$B$6:$B$23,$A82,'S8'!$E$6:$E$23,"Ambos")+SUMIFS('S9'!$I$6:$I$15,'S9'!$B$6:$B$15,$A82,'S9'!$E$6:$E$15,"Víctor")+SUMIFS('S9'!$I$6:$I$15,'S9'!$B$6:$B$15,$A82,'S9'!$E$6:$E$15,"Ambos")+SUMIFS('S10'!$I$6:$I$13,'S10'!$B$6:$B$13,$A82,'S10'!$E$6:$E$13,"Víctor")+SUMIFS('S10'!$I$6:$I$13,'S10'!$B$6:$B$13,$A82,'S10'!$E$6:$E$13,"Ambos")+SUMIFS('Holgura'!$I$6:$I$11,'Holgura'!$B$6:$B$11,$A82,'Holgura'!$E$6:$E$11,"Víctor")+SUMIFS('Holgura'!$I$6:$I$11,'Holgura'!$B$6:$B$11,$A82,'Holgura'!$E$6:$E$11,"Ambos")+SUMIFS('Entrega'!$I$6:$I$9,'Entrega'!$B$6:$B$9,$A82,'Entrega'!$E$6:$E$9,"Víctor")+SUMIFS('Entrega'!$I$6:$I$9,'Entrega'!$B$6:$B$9,$A82,'Entrega'!$E$6:$E$9,"Ambos")+SUMIFS('Defensa'!$I$6:$I$10,'Defensa'!$B$6:$B$10,$A82,'Defensa'!$E$6:$E$10,"Víctor")+SUMIFS('Defensa'!$I$6:$I$10,'Defensa'!$B$6:$B$10,$A82,'Defensa'!$E$6:$E$10,"Ambos")</f>
         <v/>
       </c>
       <c r="E82" s="21">
-        <f>SUMIFS('S1'!$I$6:$I$32,'S1'!$B$6:$B$32,$A82,'S1'!$E$6:$E$32,"Diego")+SUMIFS('S1'!$I$6:$I$32,'S1'!$B$6:$B$32,$A82,'S1'!$E$6:$E$32,"Ambos")+SUMIFS('S2'!$I$6:$I$23,'S2'!$B$6:$B$23,$A82,'S2'!$E$6:$E$23,"Diego")+SUMIFS('S2'!$I$6:$I$23,'S2'!$B$6:$B$23,$A82,'S2'!$E$6:$E$23,"Ambos")+SUMIFS('S3'!$I$6:$I$19,'S3'!$B$6:$B$19,$A82,'S3'!$E$6:$E$19,"Diego")+SUMIFS('S3'!$I$6:$I$19,'S3'!$B$6:$B$19,$A82,'S3'!$E$6:$E$19,"Ambos")+SUMIFS('S4'!$I$6:$I$20,'S4'!$B$6:$B$20,$A82,'S4'!$E$6:$E$20,"Diego")+SUMIFS('S4'!$I$6:$I$20,'S4'!$B$6:$B$20,$A82,'S4'!$E$6:$E$20,"Ambos")+SUMIFS('S5'!$I$6:$I$20,'S5'!$B$6:$B$20,$A82,'S5'!$E$6:$E$20,"Diego")+SUMIFS('S5'!$I$6:$I$20,'S5'!$B$6:$B$20,$A82,'S5'!$E$6:$E$20,"Ambos")+SUMIFS('S6'!$I$6:$I$17,'S6'!$B$6:$B$17,$A82,'S6'!$E$6:$E$17,"Diego")+SUMIFS('S6'!$I$6:$I$17,'S6'!$B$6:$B$17,$A82,'S6'!$E$6:$E$17,"Ambos")+SUMIFS('S7'!$I$6:$I$19,'S7'!$B$6:$B$19,$A82,'S7'!$E$6:$E$19,"Diego")+SUMIFS('S7'!$I$6:$I$19,'S7'!$B$6:$B$19,$A82,'S7'!$E$6:$E$19,"Ambos")+SUMIFS('S8'!$I$6:$I$23,'S8'!$B$6:$B$23,$A82,'S8'!$E$6:$E$23,"Diego")+SUMIFS('S8'!$I$6:$I$23,'S8'!$B$6:$B$23,$A82,'S8'!$E$6:$E$23,"Ambos")+SUMIFS('S9'!$I$6:$I$15,'S9'!$B$6:$B$15,$A82,'S9'!$E$6:$E$15,"Diego")+SUMIFS('S9'!$I$6:$I$15,'S9'!$B$6:$B$15,$A82,'S9'!$E$6:$E$15,"Ambos")+SUMIFS('S10'!$I$6:$I$13,'S10'!$B$6:$B$13,$A82,'S10'!$E$6:$E$13,"Diego")+SUMIFS('S10'!$I$6:$I$13,'S10'!$B$6:$B$13,$A82,'S10'!$E$6:$E$13,"Ambos")+SUMIFS('Holgura'!$I$6:$I$11,'Holgura'!$B$6:$B$11,$A82,'Holgura'!$E$6:$E$11,"Diego")+SUMIFS('Holgura'!$I$6:$I$11,'Holgura'!$B$6:$B$11,$A82,'Holgura'!$E$6:$E$11,"Ambos")+SUMIFS('Entrega'!$I$6:$I$9,'Entrega'!$B$6:$B$9,$A82,'Entrega'!$E$6:$E$9,"Diego")+SUMIFS('Entrega'!$I$6:$I$9,'Entrega'!$B$6:$B$9,$A82,'Entrega'!$E$6:$E$9,"Ambos")+SUMIFS('Defensa'!$I$6:$I$10,'Defensa'!$B$6:$B$10,$A82,'Defensa'!$E$6:$E$10,"Diego")+SUMIFS('Defensa'!$I$6:$I$10,'Defensa'!$B$6:$B$10,$A82,'Defensa'!$E$6:$E$10,"Ambos")</f>
+        <f>SUMIFS('S1'!$I$6:$I$32,'S1'!$B$6:$B$32,$A82,'S1'!$E$6:$E$32,"Diego")+SUMIFS('S1'!$I$6:$I$32,'S1'!$B$6:$B$32,$A82,'S1'!$E$6:$E$32,"Ambos")+SUMIFS('S2'!$I$6:$I$23,'S2'!$B$6:$B$23,$A82,'S2'!$E$6:$E$23,"Diego")+SUMIFS('S2'!$I$6:$I$23,'S2'!$B$6:$B$23,$A82,'S2'!$E$6:$E$23,"Ambos")+SUMIFS('S3'!$I$6:$I$24,'S3'!$B$6:$B$24,$A82,'S3'!$E$6:$E$24,"Diego")+SUMIFS('S3'!$I$6:$I$24,'S3'!$B$6:$B$24,$A82,'S3'!$E$6:$E$24,"Ambos")+SUMIFS('S4'!$I$6:$I$22,'S4'!$B$6:$B$22,$A82,'S4'!$E$6:$E$22,"Diego")+SUMIFS('S4'!$I$6:$I$22,'S4'!$B$6:$B$22,$A82,'S4'!$E$6:$E$22,"Ambos")+SUMIFS('S5'!$I$6:$I$20,'S5'!$B$6:$B$20,$A82,'S5'!$E$6:$E$20,"Diego")+SUMIFS('S5'!$I$6:$I$20,'S5'!$B$6:$B$20,$A82,'S5'!$E$6:$E$20,"Ambos")+SUMIFS('S6'!$I$6:$I$17,'S6'!$B$6:$B$17,$A82,'S6'!$E$6:$E$17,"Diego")+SUMIFS('S6'!$I$6:$I$17,'S6'!$B$6:$B$17,$A82,'S6'!$E$6:$E$17,"Ambos")+SUMIFS('S7'!$I$6:$I$19,'S7'!$B$6:$B$19,$A82,'S7'!$E$6:$E$19,"Diego")+SUMIFS('S7'!$I$6:$I$19,'S7'!$B$6:$B$19,$A82,'S7'!$E$6:$E$19,"Ambos")+SUMIFS('S8'!$I$6:$I$23,'S8'!$B$6:$B$23,$A82,'S8'!$E$6:$E$23,"Diego")+SUMIFS('S8'!$I$6:$I$23,'S8'!$B$6:$B$23,$A82,'S8'!$E$6:$E$23,"Ambos")+SUMIFS('S9'!$I$6:$I$15,'S9'!$B$6:$B$15,$A82,'S9'!$E$6:$E$15,"Diego")+SUMIFS('S9'!$I$6:$I$15,'S9'!$B$6:$B$15,$A82,'S9'!$E$6:$E$15,"Ambos")+SUMIFS('S10'!$I$6:$I$13,'S10'!$B$6:$B$13,$A82,'S10'!$E$6:$E$13,"Diego")+SUMIFS('S10'!$I$6:$I$13,'S10'!$B$6:$B$13,$A82,'S10'!$E$6:$E$13,"Ambos")+SUMIFS('Holgura'!$I$6:$I$11,'Holgura'!$B$6:$B$11,$A82,'Holgura'!$E$6:$E$11,"Diego")+SUMIFS('Holgura'!$I$6:$I$11,'Holgura'!$B$6:$B$11,$A82,'Holgura'!$E$6:$E$11,"Ambos")+SUMIFS('Entrega'!$I$6:$I$9,'Entrega'!$B$6:$B$9,$A82,'Entrega'!$E$6:$E$9,"Diego")+SUMIFS('Entrega'!$I$6:$I$9,'Entrega'!$B$6:$B$9,$A82,'Entrega'!$E$6:$E$9,"Ambos")+SUMIFS('Defensa'!$I$6:$I$10,'Defensa'!$B$6:$B$10,$A82,'Defensa'!$E$6:$E$10,"Diego")+SUMIFS('Defensa'!$I$6:$I$10,'Defensa'!$B$6:$B$10,$A82,'Defensa'!$E$6:$E$10,"Ambos")</f>
         <v/>
       </c>
       <c r="F82" s="21">
-        <f>COUNTIFS('S1'!$B$6:$B$32,$A82,'S1'!$E$6:$E$32,"Víctor")+COUNTIFS('S1'!$B$6:$B$32,$A82,'S1'!$E$6:$E$32,"Ambos")+COUNTIFS('S2'!$B$6:$B$23,$A82,'S2'!$E$6:$E$23,"Víctor")+COUNTIFS('S2'!$B$6:$B$23,$A82,'S2'!$E$6:$E$23,"Ambos")+COUNTIFS('S3'!$B$6:$B$19,$A82,'S3'!$E$6:$E$19,"Víctor")+COUNTIFS('S3'!$B$6:$B$19,$A82,'S3'!$E$6:$E$19,"Ambos")+COUNTIFS('S4'!$B$6:$B$20,$A82,'S4'!$E$6:$E$20,"Víctor")+COUNTIFS('S4'!$B$6:$B$20,$A82,'S4'!$E$6:$E$20,"Ambos")+COUNTIFS('S5'!$B$6:$B$20,$A82,'S5'!$E$6:$E$20,"Víctor")+COUNTIFS('S5'!$B$6:$B$20,$A82,'S5'!$E$6:$E$20,"Ambos")+COUNTIFS('S6'!$B$6:$B$17,$A82,'S6'!$E$6:$E$17,"Víctor")+COUNTIFS('S6'!$B$6:$B$17,$A82,'S6'!$E$6:$E$17,"Ambos")+COUNTIFS('S7'!$B$6:$B$19,$A82,'S7'!$E$6:$E$19,"Víctor")+COUNTIFS('S7'!$B$6:$B$19,$A82,'S7'!$E$6:$E$19,"Ambos")+COUNTIFS('S8'!$B$6:$B$23,$A82,'S8'!$E$6:$E$23,"Víctor")+COUNTIFS('S8'!$B$6:$B$23,$A82,'S8'!$E$6:$E$23,"Ambos")+COUNTIFS('S9'!$B$6:$B$15,$A82,'S9'!$E$6:$E$15,"Víctor")+COUNTIFS('S9'!$B$6:$B$15,$A82,'S9'!$E$6:$E$15,"Ambos")+COUNTIFS('S10'!$B$6:$B$13,$A82,'S10'!$E$6:$E$13,"Víctor")+COUNTIFS('S10'!$B$6:$B$13,$A82,'S10'!$E$6:$E$13,"Ambos")+COUNTIFS('Holgura'!$B$6:$B$11,$A82,'Holgura'!$E$6:$E$11,"Víctor")+COUNTIFS('Holgura'!$B$6:$B$11,$A82,'Holgura'!$E$6:$E$11,"Ambos")+COUNTIFS('Entrega'!$B$6:$B$9,$A82,'Entrega'!$E$6:$E$9,"Víctor")+COUNTIFS('Entrega'!$B$6:$B$9,$A82,'Entrega'!$E$6:$E$9,"Ambos")+COUNTIFS('Defensa'!$B$6:$B$10,$A82,'Defensa'!$E$6:$E$10,"Víctor")+COUNTIFS('Defensa'!$B$6:$B$10,$A82,'Defensa'!$E$6:$E$10,"Ambos")</f>
+        <f>COUNTIFS('S1'!$B$6:$B$32,$A82,'S1'!$E$6:$E$32,"Víctor")+COUNTIFS('S1'!$B$6:$B$32,$A82,'S1'!$E$6:$E$32,"Ambos")+COUNTIFS('S2'!$B$6:$B$23,$A82,'S2'!$E$6:$E$23,"Víctor")+COUNTIFS('S2'!$B$6:$B$23,$A82,'S2'!$E$6:$E$23,"Ambos")+COUNTIFS('S3'!$B$6:$B$24,$A82,'S3'!$E$6:$E$24,"Víctor")+COUNTIFS('S3'!$B$6:$B$24,$A82,'S3'!$E$6:$E$24,"Ambos")+COUNTIFS('S4'!$B$6:$B$22,$A82,'S4'!$E$6:$E$22,"Víctor")+COUNTIFS('S4'!$B$6:$B$22,$A82,'S4'!$E$6:$E$22,"Ambos")+COUNTIFS('S5'!$B$6:$B$20,$A82,'S5'!$E$6:$E$20,"Víctor")+COUNTIFS('S5'!$B$6:$B$20,$A82,'S5'!$E$6:$E$20,"Ambos")+COUNTIFS('S6'!$B$6:$B$17,$A82,'S6'!$E$6:$E$17,"Víctor")+COUNTIFS('S6'!$B$6:$B$17,$A82,'S6'!$E$6:$E$17,"Ambos")+COUNTIFS('S7'!$B$6:$B$19,$A82,'S7'!$E$6:$E$19,"Víctor")+COUNTIFS('S7'!$B$6:$B$19,$A82,'S7'!$E$6:$E$19,"Ambos")+COUNTIFS('S8'!$B$6:$B$23,$A82,'S8'!$E$6:$E$23,"Víctor")+COUNTIFS('S8'!$B$6:$B$23,$A82,'S8'!$E$6:$E$23,"Ambos")+COUNTIFS('S9'!$B$6:$B$15,$A82,'S9'!$E$6:$E$15,"Víctor")+COUNTIFS('S9'!$B$6:$B$15,$A82,'S9'!$E$6:$E$15,"Ambos")+COUNTIFS('S10'!$B$6:$B$13,$A82,'S10'!$E$6:$E$13,"Víctor")+COUNTIFS('S10'!$B$6:$B$13,$A82,'S10'!$E$6:$E$13,"Ambos")+COUNTIFS('Holgura'!$B$6:$B$11,$A82,'Holgura'!$E$6:$E$11,"Víctor")+COUNTIFS('Holgura'!$B$6:$B$11,$A82,'Holgura'!$E$6:$E$11,"Ambos")+COUNTIFS('Entrega'!$B$6:$B$9,$A82,'Entrega'!$E$6:$E$9,"Víctor")+COUNTIFS('Entrega'!$B$6:$B$9,$A82,'Entrega'!$E$6:$E$9,"Ambos")+COUNTIFS('Defensa'!$B$6:$B$10,$A82,'Defensa'!$E$6:$E$10,"Víctor")+COUNTIFS('Defensa'!$B$6:$B$10,$A82,'Defensa'!$E$6:$E$10,"Ambos")</f>
         <v/>
       </c>
       <c r="G82" s="21">
-        <f>COUNTIFS('S1'!$B$6:$B$32,$A82,'S1'!$E$6:$E$32,"Diego")+COUNTIFS('S1'!$B$6:$B$32,$A82,'S1'!$E$6:$E$32,"Ambos")+COUNTIFS('S2'!$B$6:$B$23,$A82,'S2'!$E$6:$E$23,"Diego")+COUNTIFS('S2'!$B$6:$B$23,$A82,'S2'!$E$6:$E$23,"Ambos")+COUNTIFS('S3'!$B$6:$B$19,$A82,'S3'!$E$6:$E$19,"Diego")+COUNTIFS('S3'!$B$6:$B$19,$A82,'S3'!$E$6:$E$19,"Ambos")+COUNTIFS('S4'!$B$6:$B$20,$A82,'S4'!$E$6:$E$20,"Diego")+COUNTIFS('S4'!$B$6:$B$20,$A82,'S4'!$E$6:$E$20,"Ambos")+COUNTIFS('S5'!$B$6:$B$20,$A82,'S5'!$E$6:$E$20,"Diego")+COUNTIFS('S5'!$B$6:$B$20,$A82,'S5'!$E$6:$E$20,"Ambos")+COUNTIFS('S6'!$B$6:$B$17,$A82,'S6'!$E$6:$E$17,"Diego")+COUNTIFS('S6'!$B$6:$B$17,$A82,'S6'!$E$6:$E$17,"Ambos")+COUNTIFS('S7'!$B$6:$B$19,$A82,'S7'!$E$6:$E$19,"Diego")+COUNTIFS('S7'!$B$6:$B$19,$A82,'S7'!$E$6:$E$19,"Ambos")+COUNTIFS('S8'!$B$6:$B$23,$A82,'S8'!$E$6:$E$23,"Diego")+COUNTIFS('S8'!$B$6:$B$23,$A82,'S8'!$E$6:$E$23,"Ambos")+COUNTIFS('S9'!$B$6:$B$15,$A82,'S9'!$E$6:$E$15,"Diego")+COUNTIFS('S9'!$B$6:$B$15,$A82,'S9'!$E$6:$E$15,"Ambos")+COUNTIFS('S10'!$B$6:$B$13,$A82,'S10'!$E$6:$E$13,"Diego")+COUNTIFS('S10'!$B$6:$B$13,$A82,'S10'!$E$6:$E$13,"Ambos")+COUNTIFS('Holgura'!$B$6:$B$11,$A82,'Holgura'!$E$6:$E$11,"Diego")+COUNTIFS('Holgura'!$B$6:$B$11,$A82,'Holgura'!$E$6:$E$11,"Ambos")+COUNTIFS('Entrega'!$B$6:$B$9,$A82,'Entrega'!$E$6:$E$9,"Diego")+COUNTIFS('Entrega'!$B$6:$B$9,$A82,'Entrega'!$E$6:$E$9,"Ambos")+COUNTIFS('Defensa'!$B$6:$B$10,$A82,'Defensa'!$E$6:$E$10,"Diego")+COUNTIFS('Defensa'!$B$6:$B$10,$A82,'Defensa'!$E$6:$E$10,"Ambos")</f>
+        <f>COUNTIFS('S1'!$B$6:$B$32,$A82,'S1'!$E$6:$E$32,"Diego")+COUNTIFS('S1'!$B$6:$B$32,$A82,'S1'!$E$6:$E$32,"Ambos")+COUNTIFS('S2'!$B$6:$B$23,$A82,'S2'!$E$6:$E$23,"Diego")+COUNTIFS('S2'!$B$6:$B$23,$A82,'S2'!$E$6:$E$23,"Ambos")+COUNTIFS('S3'!$B$6:$B$24,$A82,'S3'!$E$6:$E$24,"Diego")+COUNTIFS('S3'!$B$6:$B$24,$A82,'S3'!$E$6:$E$24,"Ambos")+COUNTIFS('S4'!$B$6:$B$22,$A82,'S4'!$E$6:$E$22,"Diego")+COUNTIFS('S4'!$B$6:$B$22,$A82,'S4'!$E$6:$E$22,"Ambos")+COUNTIFS('S5'!$B$6:$B$20,$A82,'S5'!$E$6:$E$20,"Diego")+COUNTIFS('S5'!$B$6:$B$20,$A82,'S5'!$E$6:$E$20,"Ambos")+COUNTIFS('S6'!$B$6:$B$17,$A82,'S6'!$E$6:$E$17,"Diego")+COUNTIFS('S6'!$B$6:$B$17,$A82,'S6'!$E$6:$E$17,"Ambos")+COUNTIFS('S7'!$B$6:$B$19,$A82,'S7'!$E$6:$E$19,"Diego")+COUNTIFS('S7'!$B$6:$B$19,$A82,'S7'!$E$6:$E$19,"Ambos")+COUNTIFS('S8'!$B$6:$B$23,$A82,'S8'!$E$6:$E$23,"Diego")+COUNTIFS('S8'!$B$6:$B$23,$A82,'S8'!$E$6:$E$23,"Ambos")+COUNTIFS('S9'!$B$6:$B$15,$A82,'S9'!$E$6:$E$15,"Diego")+COUNTIFS('S9'!$B$6:$B$15,$A82,'S9'!$E$6:$E$15,"Ambos")+COUNTIFS('S10'!$B$6:$B$13,$A82,'S10'!$E$6:$E$13,"Diego")+COUNTIFS('S10'!$B$6:$B$13,$A82,'S10'!$E$6:$E$13,"Ambos")+COUNTIFS('Holgura'!$B$6:$B$11,$A82,'Holgura'!$E$6:$E$11,"Diego")+COUNTIFS('Holgura'!$B$6:$B$11,$A82,'Holgura'!$E$6:$E$11,"Ambos")+COUNTIFS('Entrega'!$B$6:$B$9,$A82,'Entrega'!$E$6:$E$9,"Diego")+COUNTIFS('Entrega'!$B$6:$B$9,$A82,'Entrega'!$E$6:$E$9,"Ambos")+COUNTIFS('Defensa'!$B$6:$B$10,$A82,'Defensa'!$E$6:$E$10,"Diego")+COUNTIFS('Defensa'!$B$6:$B$10,$A82,'Defensa'!$E$6:$E$10,"Ambos")</f>
         <v/>
       </c>
     </row>
@@ -10942,19 +10963,19 @@
         <v/>
       </c>
       <c r="D83" s="21">
-        <f>SUMIFS('S1'!$I$6:$I$32,'S1'!$B$6:$B$32,$A83,'S1'!$E$6:$E$32,"Víctor")+SUMIFS('S1'!$I$6:$I$32,'S1'!$B$6:$B$32,$A83,'S1'!$E$6:$E$32,"Ambos")+SUMIFS('S2'!$I$6:$I$23,'S2'!$B$6:$B$23,$A83,'S2'!$E$6:$E$23,"Víctor")+SUMIFS('S2'!$I$6:$I$23,'S2'!$B$6:$B$23,$A83,'S2'!$E$6:$E$23,"Ambos")+SUMIFS('S3'!$I$6:$I$19,'S3'!$B$6:$B$19,$A83,'S3'!$E$6:$E$19,"Víctor")+SUMIFS('S3'!$I$6:$I$19,'S3'!$B$6:$B$19,$A83,'S3'!$E$6:$E$19,"Ambos")+SUMIFS('S4'!$I$6:$I$20,'S4'!$B$6:$B$20,$A83,'S4'!$E$6:$E$20,"Víctor")+SUMIFS('S4'!$I$6:$I$20,'S4'!$B$6:$B$20,$A83,'S4'!$E$6:$E$20,"Ambos")+SUMIFS('S5'!$I$6:$I$20,'S5'!$B$6:$B$20,$A83,'S5'!$E$6:$E$20,"Víctor")+SUMIFS('S5'!$I$6:$I$20,'S5'!$B$6:$B$20,$A83,'S5'!$E$6:$E$20,"Ambos")+SUMIFS('S6'!$I$6:$I$17,'S6'!$B$6:$B$17,$A83,'S6'!$E$6:$E$17,"Víctor")+SUMIFS('S6'!$I$6:$I$17,'S6'!$B$6:$B$17,$A83,'S6'!$E$6:$E$17,"Ambos")+SUMIFS('S7'!$I$6:$I$19,'S7'!$B$6:$B$19,$A83,'S7'!$E$6:$E$19,"Víctor")+SUMIFS('S7'!$I$6:$I$19,'S7'!$B$6:$B$19,$A83,'S7'!$E$6:$E$19,"Ambos")+SUMIFS('S8'!$I$6:$I$23,'S8'!$B$6:$B$23,$A83,'S8'!$E$6:$E$23,"Víctor")+SUMIFS('S8'!$I$6:$I$23,'S8'!$B$6:$B$23,$A83,'S8'!$E$6:$E$23,"Ambos")+SUMIFS('S9'!$I$6:$I$15,'S9'!$B$6:$B$15,$A83,'S9'!$E$6:$E$15,"Víctor")+SUMIFS('S9'!$I$6:$I$15,'S9'!$B$6:$B$15,$A83,'S9'!$E$6:$E$15,"Ambos")+SUMIFS('S10'!$I$6:$I$13,'S10'!$B$6:$B$13,$A83,'S10'!$E$6:$E$13,"Víctor")+SUMIFS('S10'!$I$6:$I$13,'S10'!$B$6:$B$13,$A83,'S10'!$E$6:$E$13,"Ambos")+SUMIFS('Holgura'!$I$6:$I$11,'Holgura'!$B$6:$B$11,$A83,'Holgura'!$E$6:$E$11,"Víctor")+SUMIFS('Holgura'!$I$6:$I$11,'Holgura'!$B$6:$B$11,$A83,'Holgura'!$E$6:$E$11,"Ambos")+SUMIFS('Entrega'!$I$6:$I$9,'Entrega'!$B$6:$B$9,$A83,'Entrega'!$E$6:$E$9,"Víctor")+SUMIFS('Entrega'!$I$6:$I$9,'Entrega'!$B$6:$B$9,$A83,'Entrega'!$E$6:$E$9,"Ambos")+SUMIFS('Defensa'!$I$6:$I$10,'Defensa'!$B$6:$B$10,$A83,'Defensa'!$E$6:$E$10,"Víctor")+SUMIFS('Defensa'!$I$6:$I$10,'Defensa'!$B$6:$B$10,$A83,'Defensa'!$E$6:$E$10,"Ambos")</f>
+        <f>SUMIFS('S1'!$I$6:$I$32,'S1'!$B$6:$B$32,$A83,'S1'!$E$6:$E$32,"Víctor")+SUMIFS('S1'!$I$6:$I$32,'S1'!$B$6:$B$32,$A83,'S1'!$E$6:$E$32,"Ambos")+SUMIFS('S2'!$I$6:$I$23,'S2'!$B$6:$B$23,$A83,'S2'!$E$6:$E$23,"Víctor")+SUMIFS('S2'!$I$6:$I$23,'S2'!$B$6:$B$23,$A83,'S2'!$E$6:$E$23,"Ambos")+SUMIFS('S3'!$I$6:$I$24,'S3'!$B$6:$B$24,$A83,'S3'!$E$6:$E$24,"Víctor")+SUMIFS('S3'!$I$6:$I$24,'S3'!$B$6:$B$24,$A83,'S3'!$E$6:$E$24,"Ambos")+SUMIFS('S4'!$I$6:$I$22,'S4'!$B$6:$B$22,$A83,'S4'!$E$6:$E$22,"Víctor")+SUMIFS('S4'!$I$6:$I$22,'S4'!$B$6:$B$22,$A83,'S4'!$E$6:$E$22,"Ambos")+SUMIFS('S5'!$I$6:$I$20,'S5'!$B$6:$B$20,$A83,'S5'!$E$6:$E$20,"Víctor")+SUMIFS('S5'!$I$6:$I$20,'S5'!$B$6:$B$20,$A83,'S5'!$E$6:$E$20,"Ambos")+SUMIFS('S6'!$I$6:$I$17,'S6'!$B$6:$B$17,$A83,'S6'!$E$6:$E$17,"Víctor")+SUMIFS('S6'!$I$6:$I$17,'S6'!$B$6:$B$17,$A83,'S6'!$E$6:$E$17,"Ambos")+SUMIFS('S7'!$I$6:$I$19,'S7'!$B$6:$B$19,$A83,'S7'!$E$6:$E$19,"Víctor")+SUMIFS('S7'!$I$6:$I$19,'S7'!$B$6:$B$19,$A83,'S7'!$E$6:$E$19,"Ambos")+SUMIFS('S8'!$I$6:$I$23,'S8'!$B$6:$B$23,$A83,'S8'!$E$6:$E$23,"Víctor")+SUMIFS('S8'!$I$6:$I$23,'S8'!$B$6:$B$23,$A83,'S8'!$E$6:$E$23,"Ambos")+SUMIFS('S9'!$I$6:$I$15,'S9'!$B$6:$B$15,$A83,'S9'!$E$6:$E$15,"Víctor")+SUMIFS('S9'!$I$6:$I$15,'S9'!$B$6:$B$15,$A83,'S9'!$E$6:$E$15,"Ambos")+SUMIFS('S10'!$I$6:$I$13,'S10'!$B$6:$B$13,$A83,'S10'!$E$6:$E$13,"Víctor")+SUMIFS('S10'!$I$6:$I$13,'S10'!$B$6:$B$13,$A83,'S10'!$E$6:$E$13,"Ambos")+SUMIFS('Holgura'!$I$6:$I$11,'Holgura'!$B$6:$B$11,$A83,'Holgura'!$E$6:$E$11,"Víctor")+SUMIFS('Holgura'!$I$6:$I$11,'Holgura'!$B$6:$B$11,$A83,'Holgura'!$E$6:$E$11,"Ambos")+SUMIFS('Entrega'!$I$6:$I$9,'Entrega'!$B$6:$B$9,$A83,'Entrega'!$E$6:$E$9,"Víctor")+SUMIFS('Entrega'!$I$6:$I$9,'Entrega'!$B$6:$B$9,$A83,'Entrega'!$E$6:$E$9,"Ambos")+SUMIFS('Defensa'!$I$6:$I$10,'Defensa'!$B$6:$B$10,$A83,'Defensa'!$E$6:$E$10,"Víctor")+SUMIFS('Defensa'!$I$6:$I$10,'Defensa'!$B$6:$B$10,$A83,'Defensa'!$E$6:$E$10,"Ambos")</f>
         <v/>
       </c>
       <c r="E83" s="21">
-        <f>SUMIFS('S1'!$I$6:$I$32,'S1'!$B$6:$B$32,$A83,'S1'!$E$6:$E$32,"Diego")+SUMIFS('S1'!$I$6:$I$32,'S1'!$B$6:$B$32,$A83,'S1'!$E$6:$E$32,"Ambos")+SUMIFS('S2'!$I$6:$I$23,'S2'!$B$6:$B$23,$A83,'S2'!$E$6:$E$23,"Diego")+SUMIFS('S2'!$I$6:$I$23,'S2'!$B$6:$B$23,$A83,'S2'!$E$6:$E$23,"Ambos")+SUMIFS('S3'!$I$6:$I$19,'S3'!$B$6:$B$19,$A83,'S3'!$E$6:$E$19,"Diego")+SUMIFS('S3'!$I$6:$I$19,'S3'!$B$6:$B$19,$A83,'S3'!$E$6:$E$19,"Ambos")+SUMIFS('S4'!$I$6:$I$20,'S4'!$B$6:$B$20,$A83,'S4'!$E$6:$E$20,"Diego")+SUMIFS('S4'!$I$6:$I$20,'S4'!$B$6:$B$20,$A83,'S4'!$E$6:$E$20,"Ambos")+SUMIFS('S5'!$I$6:$I$20,'S5'!$B$6:$B$20,$A83,'S5'!$E$6:$E$20,"Diego")+SUMIFS('S5'!$I$6:$I$20,'S5'!$B$6:$B$20,$A83,'S5'!$E$6:$E$20,"Ambos")+SUMIFS('S6'!$I$6:$I$17,'S6'!$B$6:$B$17,$A83,'S6'!$E$6:$E$17,"Diego")+SUMIFS('S6'!$I$6:$I$17,'S6'!$B$6:$B$17,$A83,'S6'!$E$6:$E$17,"Ambos")+SUMIFS('S7'!$I$6:$I$19,'S7'!$B$6:$B$19,$A83,'S7'!$E$6:$E$19,"Diego")+SUMIFS('S7'!$I$6:$I$19,'S7'!$B$6:$B$19,$A83,'S7'!$E$6:$E$19,"Ambos")+SUMIFS('S8'!$I$6:$I$23,'S8'!$B$6:$B$23,$A83,'S8'!$E$6:$E$23,"Diego")+SUMIFS('S8'!$I$6:$I$23,'S8'!$B$6:$B$23,$A83,'S8'!$E$6:$E$23,"Ambos")+SUMIFS('S9'!$I$6:$I$15,'S9'!$B$6:$B$15,$A83,'S9'!$E$6:$E$15,"Diego")+SUMIFS('S9'!$I$6:$I$15,'S9'!$B$6:$B$15,$A83,'S9'!$E$6:$E$15,"Ambos")+SUMIFS('S10'!$I$6:$I$13,'S10'!$B$6:$B$13,$A83,'S10'!$E$6:$E$13,"Diego")+SUMIFS('S10'!$I$6:$I$13,'S10'!$B$6:$B$13,$A83,'S10'!$E$6:$E$13,"Ambos")+SUMIFS('Holgura'!$I$6:$I$11,'Holgura'!$B$6:$B$11,$A83,'Holgura'!$E$6:$E$11,"Diego")+SUMIFS('Holgura'!$I$6:$I$11,'Holgura'!$B$6:$B$11,$A83,'Holgura'!$E$6:$E$11,"Ambos")+SUMIFS('Entrega'!$I$6:$I$9,'Entrega'!$B$6:$B$9,$A83,'Entrega'!$E$6:$E$9,"Diego")+SUMIFS('Entrega'!$I$6:$I$9,'Entrega'!$B$6:$B$9,$A83,'Entrega'!$E$6:$E$9,"Ambos")+SUMIFS('Defensa'!$I$6:$I$10,'Defensa'!$B$6:$B$10,$A83,'Defensa'!$E$6:$E$10,"Diego")+SUMIFS('Defensa'!$I$6:$I$10,'Defensa'!$B$6:$B$10,$A83,'Defensa'!$E$6:$E$10,"Ambos")</f>
+        <f>SUMIFS('S1'!$I$6:$I$32,'S1'!$B$6:$B$32,$A83,'S1'!$E$6:$E$32,"Diego")+SUMIFS('S1'!$I$6:$I$32,'S1'!$B$6:$B$32,$A83,'S1'!$E$6:$E$32,"Ambos")+SUMIFS('S2'!$I$6:$I$23,'S2'!$B$6:$B$23,$A83,'S2'!$E$6:$E$23,"Diego")+SUMIFS('S2'!$I$6:$I$23,'S2'!$B$6:$B$23,$A83,'S2'!$E$6:$E$23,"Ambos")+SUMIFS('S3'!$I$6:$I$24,'S3'!$B$6:$B$24,$A83,'S3'!$E$6:$E$24,"Diego")+SUMIFS('S3'!$I$6:$I$24,'S3'!$B$6:$B$24,$A83,'S3'!$E$6:$E$24,"Ambos")+SUMIFS('S4'!$I$6:$I$22,'S4'!$B$6:$B$22,$A83,'S4'!$E$6:$E$22,"Diego")+SUMIFS('S4'!$I$6:$I$22,'S4'!$B$6:$B$22,$A83,'S4'!$E$6:$E$22,"Ambos")+SUMIFS('S5'!$I$6:$I$20,'S5'!$B$6:$B$20,$A83,'S5'!$E$6:$E$20,"Diego")+SUMIFS('S5'!$I$6:$I$20,'S5'!$B$6:$B$20,$A83,'S5'!$E$6:$E$20,"Ambos")+SUMIFS('S6'!$I$6:$I$17,'S6'!$B$6:$B$17,$A83,'S6'!$E$6:$E$17,"Diego")+SUMIFS('S6'!$I$6:$I$17,'S6'!$B$6:$B$17,$A83,'S6'!$E$6:$E$17,"Ambos")+SUMIFS('S7'!$I$6:$I$19,'S7'!$B$6:$B$19,$A83,'S7'!$E$6:$E$19,"Diego")+SUMIFS('S7'!$I$6:$I$19,'S7'!$B$6:$B$19,$A83,'S7'!$E$6:$E$19,"Ambos")+SUMIFS('S8'!$I$6:$I$23,'S8'!$B$6:$B$23,$A83,'S8'!$E$6:$E$23,"Diego")+SUMIFS('S8'!$I$6:$I$23,'S8'!$B$6:$B$23,$A83,'S8'!$E$6:$E$23,"Ambos")+SUMIFS('S9'!$I$6:$I$15,'S9'!$B$6:$B$15,$A83,'S9'!$E$6:$E$15,"Diego")+SUMIFS('S9'!$I$6:$I$15,'S9'!$B$6:$B$15,$A83,'S9'!$E$6:$E$15,"Ambos")+SUMIFS('S10'!$I$6:$I$13,'S10'!$B$6:$B$13,$A83,'S10'!$E$6:$E$13,"Diego")+SUMIFS('S10'!$I$6:$I$13,'S10'!$B$6:$B$13,$A83,'S10'!$E$6:$E$13,"Ambos")+SUMIFS('Holgura'!$I$6:$I$11,'Holgura'!$B$6:$B$11,$A83,'Holgura'!$E$6:$E$11,"Diego")+SUMIFS('Holgura'!$I$6:$I$11,'Holgura'!$B$6:$B$11,$A83,'Holgura'!$E$6:$E$11,"Ambos")+SUMIFS('Entrega'!$I$6:$I$9,'Entrega'!$B$6:$B$9,$A83,'Entrega'!$E$6:$E$9,"Diego")+SUMIFS('Entrega'!$I$6:$I$9,'Entrega'!$B$6:$B$9,$A83,'Entrega'!$E$6:$E$9,"Ambos")+SUMIFS('Defensa'!$I$6:$I$10,'Defensa'!$B$6:$B$10,$A83,'Defensa'!$E$6:$E$10,"Diego")+SUMIFS('Defensa'!$I$6:$I$10,'Defensa'!$B$6:$B$10,$A83,'Defensa'!$E$6:$E$10,"Ambos")</f>
         <v/>
       </c>
       <c r="F83" s="21">
-        <f>COUNTIFS('S1'!$B$6:$B$32,$A83,'S1'!$E$6:$E$32,"Víctor")+COUNTIFS('S1'!$B$6:$B$32,$A83,'S1'!$E$6:$E$32,"Ambos")+COUNTIFS('S2'!$B$6:$B$23,$A83,'S2'!$E$6:$E$23,"Víctor")+COUNTIFS('S2'!$B$6:$B$23,$A83,'S2'!$E$6:$E$23,"Ambos")+COUNTIFS('S3'!$B$6:$B$19,$A83,'S3'!$E$6:$E$19,"Víctor")+COUNTIFS('S3'!$B$6:$B$19,$A83,'S3'!$E$6:$E$19,"Ambos")+COUNTIFS('S4'!$B$6:$B$20,$A83,'S4'!$E$6:$E$20,"Víctor")+COUNTIFS('S4'!$B$6:$B$20,$A83,'S4'!$E$6:$E$20,"Ambos")+COUNTIFS('S5'!$B$6:$B$20,$A83,'S5'!$E$6:$E$20,"Víctor")+COUNTIFS('S5'!$B$6:$B$20,$A83,'S5'!$E$6:$E$20,"Ambos")+COUNTIFS('S6'!$B$6:$B$17,$A83,'S6'!$E$6:$E$17,"Víctor")+COUNTIFS('S6'!$B$6:$B$17,$A83,'S6'!$E$6:$E$17,"Ambos")+COUNTIFS('S7'!$B$6:$B$19,$A83,'S7'!$E$6:$E$19,"Víctor")+COUNTIFS('S7'!$B$6:$B$19,$A83,'S7'!$E$6:$E$19,"Ambos")+COUNTIFS('S8'!$B$6:$B$23,$A83,'S8'!$E$6:$E$23,"Víctor")+COUNTIFS('S8'!$B$6:$B$23,$A83,'S8'!$E$6:$E$23,"Ambos")+COUNTIFS('S9'!$B$6:$B$15,$A83,'S9'!$E$6:$E$15,"Víctor")+COUNTIFS('S9'!$B$6:$B$15,$A83,'S9'!$E$6:$E$15,"Ambos")+COUNTIFS('S10'!$B$6:$B$13,$A83,'S10'!$E$6:$E$13,"Víctor")+COUNTIFS('S10'!$B$6:$B$13,$A83,'S10'!$E$6:$E$13,"Ambos")+COUNTIFS('Holgura'!$B$6:$B$11,$A83,'Holgura'!$E$6:$E$11,"Víctor")+COUNTIFS('Holgura'!$B$6:$B$11,$A83,'Holgura'!$E$6:$E$11,"Ambos")+COUNTIFS('Entrega'!$B$6:$B$9,$A83,'Entrega'!$E$6:$E$9,"Víctor")+COUNTIFS('Entrega'!$B$6:$B$9,$A83,'Entrega'!$E$6:$E$9,"Ambos")+COUNTIFS('Defensa'!$B$6:$B$10,$A83,'Defensa'!$E$6:$E$10,"Víctor")+COUNTIFS('Defensa'!$B$6:$B$10,$A83,'Defensa'!$E$6:$E$10,"Ambos")</f>
+        <f>COUNTIFS('S1'!$B$6:$B$32,$A83,'S1'!$E$6:$E$32,"Víctor")+COUNTIFS('S1'!$B$6:$B$32,$A83,'S1'!$E$6:$E$32,"Ambos")+COUNTIFS('S2'!$B$6:$B$23,$A83,'S2'!$E$6:$E$23,"Víctor")+COUNTIFS('S2'!$B$6:$B$23,$A83,'S2'!$E$6:$E$23,"Ambos")+COUNTIFS('S3'!$B$6:$B$24,$A83,'S3'!$E$6:$E$24,"Víctor")+COUNTIFS('S3'!$B$6:$B$24,$A83,'S3'!$E$6:$E$24,"Ambos")+COUNTIFS('S4'!$B$6:$B$22,$A83,'S4'!$E$6:$E$22,"Víctor")+COUNTIFS('S4'!$B$6:$B$22,$A83,'S4'!$E$6:$E$22,"Ambos")+COUNTIFS('S5'!$B$6:$B$20,$A83,'S5'!$E$6:$E$20,"Víctor")+COUNTIFS('S5'!$B$6:$B$20,$A83,'S5'!$E$6:$E$20,"Ambos")+COUNTIFS('S6'!$B$6:$B$17,$A83,'S6'!$E$6:$E$17,"Víctor")+COUNTIFS('S6'!$B$6:$B$17,$A83,'S6'!$E$6:$E$17,"Ambos")+COUNTIFS('S7'!$B$6:$B$19,$A83,'S7'!$E$6:$E$19,"Víctor")+COUNTIFS('S7'!$B$6:$B$19,$A83,'S7'!$E$6:$E$19,"Ambos")+COUNTIFS('S8'!$B$6:$B$23,$A83,'S8'!$E$6:$E$23,"Víctor")+COUNTIFS('S8'!$B$6:$B$23,$A83,'S8'!$E$6:$E$23,"Ambos")+COUNTIFS('S9'!$B$6:$B$15,$A83,'S9'!$E$6:$E$15,"Víctor")+COUNTIFS('S9'!$B$6:$B$15,$A83,'S9'!$E$6:$E$15,"Ambos")+COUNTIFS('S10'!$B$6:$B$13,$A83,'S10'!$E$6:$E$13,"Víctor")+COUNTIFS('S10'!$B$6:$B$13,$A83,'S10'!$E$6:$E$13,"Ambos")+COUNTIFS('Holgura'!$B$6:$B$11,$A83,'Holgura'!$E$6:$E$11,"Víctor")+COUNTIFS('Holgura'!$B$6:$B$11,$A83,'Holgura'!$E$6:$E$11,"Ambos")+COUNTIFS('Entrega'!$B$6:$B$9,$A83,'Entrega'!$E$6:$E$9,"Víctor")+COUNTIFS('Entrega'!$B$6:$B$9,$A83,'Entrega'!$E$6:$E$9,"Ambos")+COUNTIFS('Defensa'!$B$6:$B$10,$A83,'Defensa'!$E$6:$E$10,"Víctor")+COUNTIFS('Defensa'!$B$6:$B$10,$A83,'Defensa'!$E$6:$E$10,"Ambos")</f>
         <v/>
       </c>
       <c r="G83" s="21">
-        <f>COUNTIFS('S1'!$B$6:$B$32,$A83,'S1'!$E$6:$E$32,"Diego")+COUNTIFS('S1'!$B$6:$B$32,$A83,'S1'!$E$6:$E$32,"Ambos")+COUNTIFS('S2'!$B$6:$B$23,$A83,'S2'!$E$6:$E$23,"Diego")+COUNTIFS('S2'!$B$6:$B$23,$A83,'S2'!$E$6:$E$23,"Ambos")+COUNTIFS('S3'!$B$6:$B$19,$A83,'S3'!$E$6:$E$19,"Diego")+COUNTIFS('S3'!$B$6:$B$19,$A83,'S3'!$E$6:$E$19,"Ambos")+COUNTIFS('S4'!$B$6:$B$20,$A83,'S4'!$E$6:$E$20,"Diego")+COUNTIFS('S4'!$B$6:$B$20,$A83,'S4'!$E$6:$E$20,"Ambos")+COUNTIFS('S5'!$B$6:$B$20,$A83,'S5'!$E$6:$E$20,"Diego")+COUNTIFS('S5'!$B$6:$B$20,$A83,'S5'!$E$6:$E$20,"Ambos")+COUNTIFS('S6'!$B$6:$B$17,$A83,'S6'!$E$6:$E$17,"Diego")+COUNTIFS('S6'!$B$6:$B$17,$A83,'S6'!$E$6:$E$17,"Ambos")+COUNTIFS('S7'!$B$6:$B$19,$A83,'S7'!$E$6:$E$19,"Diego")+COUNTIFS('S7'!$B$6:$B$19,$A83,'S7'!$E$6:$E$19,"Ambos")+COUNTIFS('S8'!$B$6:$B$23,$A83,'S8'!$E$6:$E$23,"Diego")+COUNTIFS('S8'!$B$6:$B$23,$A83,'S8'!$E$6:$E$23,"Ambos")+COUNTIFS('S9'!$B$6:$B$15,$A83,'S9'!$E$6:$E$15,"Diego")+COUNTIFS('S9'!$B$6:$B$15,$A83,'S9'!$E$6:$E$15,"Ambos")+COUNTIFS('S10'!$B$6:$B$13,$A83,'S10'!$E$6:$E$13,"Diego")+COUNTIFS('S10'!$B$6:$B$13,$A83,'S10'!$E$6:$E$13,"Ambos")+COUNTIFS('Holgura'!$B$6:$B$11,$A83,'Holgura'!$E$6:$E$11,"Diego")+COUNTIFS('Holgura'!$B$6:$B$11,$A83,'Holgura'!$E$6:$E$11,"Ambos")+COUNTIFS('Entrega'!$B$6:$B$9,$A83,'Entrega'!$E$6:$E$9,"Diego")+COUNTIFS('Entrega'!$B$6:$B$9,$A83,'Entrega'!$E$6:$E$9,"Ambos")+COUNTIFS('Defensa'!$B$6:$B$10,$A83,'Defensa'!$E$6:$E$10,"Diego")+COUNTIFS('Defensa'!$B$6:$B$10,$A83,'Defensa'!$E$6:$E$10,"Ambos")</f>
+        <f>COUNTIFS('S1'!$B$6:$B$32,$A83,'S1'!$E$6:$E$32,"Diego")+COUNTIFS('S1'!$B$6:$B$32,$A83,'S1'!$E$6:$E$32,"Ambos")+COUNTIFS('S2'!$B$6:$B$23,$A83,'S2'!$E$6:$E$23,"Diego")+COUNTIFS('S2'!$B$6:$B$23,$A83,'S2'!$E$6:$E$23,"Ambos")+COUNTIFS('S3'!$B$6:$B$24,$A83,'S3'!$E$6:$E$24,"Diego")+COUNTIFS('S3'!$B$6:$B$24,$A83,'S3'!$E$6:$E$24,"Ambos")+COUNTIFS('S4'!$B$6:$B$22,$A83,'S4'!$E$6:$E$22,"Diego")+COUNTIFS('S4'!$B$6:$B$22,$A83,'S4'!$E$6:$E$22,"Ambos")+COUNTIFS('S5'!$B$6:$B$20,$A83,'S5'!$E$6:$E$20,"Diego")+COUNTIFS('S5'!$B$6:$B$20,$A83,'S5'!$E$6:$E$20,"Ambos")+COUNTIFS('S6'!$B$6:$B$17,$A83,'S6'!$E$6:$E$17,"Diego")+COUNTIFS('S6'!$B$6:$B$17,$A83,'S6'!$E$6:$E$17,"Ambos")+COUNTIFS('S7'!$B$6:$B$19,$A83,'S7'!$E$6:$E$19,"Diego")+COUNTIFS('S7'!$B$6:$B$19,$A83,'S7'!$E$6:$E$19,"Ambos")+COUNTIFS('S8'!$B$6:$B$23,$A83,'S8'!$E$6:$E$23,"Diego")+COUNTIFS('S8'!$B$6:$B$23,$A83,'S8'!$E$6:$E$23,"Ambos")+COUNTIFS('S9'!$B$6:$B$15,$A83,'S9'!$E$6:$E$15,"Diego")+COUNTIFS('S9'!$B$6:$B$15,$A83,'S9'!$E$6:$E$15,"Ambos")+COUNTIFS('S10'!$B$6:$B$13,$A83,'S10'!$E$6:$E$13,"Diego")+COUNTIFS('S10'!$B$6:$B$13,$A83,'S10'!$E$6:$E$13,"Ambos")+COUNTIFS('Holgura'!$B$6:$B$11,$A83,'Holgura'!$E$6:$E$11,"Diego")+COUNTIFS('Holgura'!$B$6:$B$11,$A83,'Holgura'!$E$6:$E$11,"Ambos")+COUNTIFS('Entrega'!$B$6:$B$9,$A83,'Entrega'!$E$6:$E$9,"Diego")+COUNTIFS('Entrega'!$B$6:$B$9,$A83,'Entrega'!$E$6:$E$9,"Ambos")+COUNTIFS('Defensa'!$B$6:$B$10,$A83,'Defensa'!$E$6:$E$10,"Diego")+COUNTIFS('Defensa'!$B$6:$B$10,$A83,'Defensa'!$E$6:$E$10,"Ambos")</f>
         <v/>
       </c>
     </row>
@@ -10971,19 +10992,19 @@
         <v/>
       </c>
       <c r="D84" s="21">
-        <f>SUMIFS('S1'!$I$6:$I$32,'S1'!$B$6:$B$32,$A84,'S1'!$E$6:$E$32,"Víctor")+SUMIFS('S1'!$I$6:$I$32,'S1'!$B$6:$B$32,$A84,'S1'!$E$6:$E$32,"Ambos")+SUMIFS('S2'!$I$6:$I$23,'S2'!$B$6:$B$23,$A84,'S2'!$E$6:$E$23,"Víctor")+SUMIFS('S2'!$I$6:$I$23,'S2'!$B$6:$B$23,$A84,'S2'!$E$6:$E$23,"Ambos")+SUMIFS('S3'!$I$6:$I$19,'S3'!$B$6:$B$19,$A84,'S3'!$E$6:$E$19,"Víctor")+SUMIFS('S3'!$I$6:$I$19,'S3'!$B$6:$B$19,$A84,'S3'!$E$6:$E$19,"Ambos")+SUMIFS('S4'!$I$6:$I$20,'S4'!$B$6:$B$20,$A84,'S4'!$E$6:$E$20,"Víctor")+SUMIFS('S4'!$I$6:$I$20,'S4'!$B$6:$B$20,$A84,'S4'!$E$6:$E$20,"Ambos")+SUMIFS('S5'!$I$6:$I$20,'S5'!$B$6:$B$20,$A84,'S5'!$E$6:$E$20,"Víctor")+SUMIFS('S5'!$I$6:$I$20,'S5'!$B$6:$B$20,$A84,'S5'!$E$6:$E$20,"Ambos")+SUMIFS('S6'!$I$6:$I$17,'S6'!$B$6:$B$17,$A84,'S6'!$E$6:$E$17,"Víctor")+SUMIFS('S6'!$I$6:$I$17,'S6'!$B$6:$B$17,$A84,'S6'!$E$6:$E$17,"Ambos")+SUMIFS('S7'!$I$6:$I$19,'S7'!$B$6:$B$19,$A84,'S7'!$E$6:$E$19,"Víctor")+SUMIFS('S7'!$I$6:$I$19,'S7'!$B$6:$B$19,$A84,'S7'!$E$6:$E$19,"Ambos")+SUMIFS('S8'!$I$6:$I$23,'S8'!$B$6:$B$23,$A84,'S8'!$E$6:$E$23,"Víctor")+SUMIFS('S8'!$I$6:$I$23,'S8'!$B$6:$B$23,$A84,'S8'!$E$6:$E$23,"Ambos")+SUMIFS('S9'!$I$6:$I$15,'S9'!$B$6:$B$15,$A84,'S9'!$E$6:$E$15,"Víctor")+SUMIFS('S9'!$I$6:$I$15,'S9'!$B$6:$B$15,$A84,'S9'!$E$6:$E$15,"Ambos")+SUMIFS('S10'!$I$6:$I$13,'S10'!$B$6:$B$13,$A84,'S10'!$E$6:$E$13,"Víctor")+SUMIFS('S10'!$I$6:$I$13,'S10'!$B$6:$B$13,$A84,'S10'!$E$6:$E$13,"Ambos")+SUMIFS('Holgura'!$I$6:$I$11,'Holgura'!$B$6:$B$11,$A84,'Holgura'!$E$6:$E$11,"Víctor")+SUMIFS('Holgura'!$I$6:$I$11,'Holgura'!$B$6:$B$11,$A84,'Holgura'!$E$6:$E$11,"Ambos")+SUMIFS('Entrega'!$I$6:$I$9,'Entrega'!$B$6:$B$9,$A84,'Entrega'!$E$6:$E$9,"Víctor")+SUMIFS('Entrega'!$I$6:$I$9,'Entrega'!$B$6:$B$9,$A84,'Entrega'!$E$6:$E$9,"Ambos")+SUMIFS('Defensa'!$I$6:$I$10,'Defensa'!$B$6:$B$10,$A84,'Defensa'!$E$6:$E$10,"Víctor")+SUMIFS('Defensa'!$I$6:$I$10,'Defensa'!$B$6:$B$10,$A84,'Defensa'!$E$6:$E$10,"Ambos")</f>
+        <f>SUMIFS('S1'!$I$6:$I$32,'S1'!$B$6:$B$32,$A84,'S1'!$E$6:$E$32,"Víctor")+SUMIFS('S1'!$I$6:$I$32,'S1'!$B$6:$B$32,$A84,'S1'!$E$6:$E$32,"Ambos")+SUMIFS('S2'!$I$6:$I$23,'S2'!$B$6:$B$23,$A84,'S2'!$E$6:$E$23,"Víctor")+SUMIFS('S2'!$I$6:$I$23,'S2'!$B$6:$B$23,$A84,'S2'!$E$6:$E$23,"Ambos")+SUMIFS('S3'!$I$6:$I$24,'S3'!$B$6:$B$24,$A84,'S3'!$E$6:$E$24,"Víctor")+SUMIFS('S3'!$I$6:$I$24,'S3'!$B$6:$B$24,$A84,'S3'!$E$6:$E$24,"Ambos")+SUMIFS('S4'!$I$6:$I$22,'S4'!$B$6:$B$22,$A84,'S4'!$E$6:$E$22,"Víctor")+SUMIFS('S4'!$I$6:$I$22,'S4'!$B$6:$B$22,$A84,'S4'!$E$6:$E$22,"Ambos")+SUMIFS('S5'!$I$6:$I$20,'S5'!$B$6:$B$20,$A84,'S5'!$E$6:$E$20,"Víctor")+SUMIFS('S5'!$I$6:$I$20,'S5'!$B$6:$B$20,$A84,'S5'!$E$6:$E$20,"Ambos")+SUMIFS('S6'!$I$6:$I$17,'S6'!$B$6:$B$17,$A84,'S6'!$E$6:$E$17,"Víctor")+SUMIFS('S6'!$I$6:$I$17,'S6'!$B$6:$B$17,$A84,'S6'!$E$6:$E$17,"Ambos")+SUMIFS('S7'!$I$6:$I$19,'S7'!$B$6:$B$19,$A84,'S7'!$E$6:$E$19,"Víctor")+SUMIFS('S7'!$I$6:$I$19,'S7'!$B$6:$B$19,$A84,'S7'!$E$6:$E$19,"Ambos")+SUMIFS('S8'!$I$6:$I$23,'S8'!$B$6:$B$23,$A84,'S8'!$E$6:$E$23,"Víctor")+SUMIFS('S8'!$I$6:$I$23,'S8'!$B$6:$B$23,$A84,'S8'!$E$6:$E$23,"Ambos")+SUMIFS('S9'!$I$6:$I$15,'S9'!$B$6:$B$15,$A84,'S9'!$E$6:$E$15,"Víctor")+SUMIFS('S9'!$I$6:$I$15,'S9'!$B$6:$B$15,$A84,'S9'!$E$6:$E$15,"Ambos")+SUMIFS('S10'!$I$6:$I$13,'S10'!$B$6:$B$13,$A84,'S10'!$E$6:$E$13,"Víctor")+SUMIFS('S10'!$I$6:$I$13,'S10'!$B$6:$B$13,$A84,'S10'!$E$6:$E$13,"Ambos")+SUMIFS('Holgura'!$I$6:$I$11,'Holgura'!$B$6:$B$11,$A84,'Holgura'!$E$6:$E$11,"Víctor")+SUMIFS('Holgura'!$I$6:$I$11,'Holgura'!$B$6:$B$11,$A84,'Holgura'!$E$6:$E$11,"Ambos")+SUMIFS('Entrega'!$I$6:$I$9,'Entrega'!$B$6:$B$9,$A84,'Entrega'!$E$6:$E$9,"Víctor")+SUMIFS('Entrega'!$I$6:$I$9,'Entrega'!$B$6:$B$9,$A84,'Entrega'!$E$6:$E$9,"Ambos")+SUMIFS('Defensa'!$I$6:$I$10,'Defensa'!$B$6:$B$10,$A84,'Defensa'!$E$6:$E$10,"Víctor")+SUMIFS('Defensa'!$I$6:$I$10,'Defensa'!$B$6:$B$10,$A84,'Defensa'!$E$6:$E$10,"Ambos")</f>
         <v/>
       </c>
       <c r="E84" s="21">
-        <f>SUMIFS('S1'!$I$6:$I$32,'S1'!$B$6:$B$32,$A84,'S1'!$E$6:$E$32,"Diego")+SUMIFS('S1'!$I$6:$I$32,'S1'!$B$6:$B$32,$A84,'S1'!$E$6:$E$32,"Ambos")+SUMIFS('S2'!$I$6:$I$23,'S2'!$B$6:$B$23,$A84,'S2'!$E$6:$E$23,"Diego")+SUMIFS('S2'!$I$6:$I$23,'S2'!$B$6:$B$23,$A84,'S2'!$E$6:$E$23,"Ambos")+SUMIFS('S3'!$I$6:$I$19,'S3'!$B$6:$B$19,$A84,'S3'!$E$6:$E$19,"Diego")+SUMIFS('S3'!$I$6:$I$19,'S3'!$B$6:$B$19,$A84,'S3'!$E$6:$E$19,"Ambos")+SUMIFS('S4'!$I$6:$I$20,'S4'!$B$6:$B$20,$A84,'S4'!$E$6:$E$20,"Diego")+SUMIFS('S4'!$I$6:$I$20,'S4'!$B$6:$B$20,$A84,'S4'!$E$6:$E$20,"Ambos")+SUMIFS('S5'!$I$6:$I$20,'S5'!$B$6:$B$20,$A84,'S5'!$E$6:$E$20,"Diego")+SUMIFS('S5'!$I$6:$I$20,'S5'!$B$6:$B$20,$A84,'S5'!$E$6:$E$20,"Ambos")+SUMIFS('S6'!$I$6:$I$17,'S6'!$B$6:$B$17,$A84,'S6'!$E$6:$E$17,"Diego")+SUMIFS('S6'!$I$6:$I$17,'S6'!$B$6:$B$17,$A84,'S6'!$E$6:$E$17,"Ambos")+SUMIFS('S7'!$I$6:$I$19,'S7'!$B$6:$B$19,$A84,'S7'!$E$6:$E$19,"Diego")+SUMIFS('S7'!$I$6:$I$19,'S7'!$B$6:$B$19,$A84,'S7'!$E$6:$E$19,"Ambos")+SUMIFS('S8'!$I$6:$I$23,'S8'!$B$6:$B$23,$A84,'S8'!$E$6:$E$23,"Diego")+SUMIFS('S8'!$I$6:$I$23,'S8'!$B$6:$B$23,$A84,'S8'!$E$6:$E$23,"Ambos")+SUMIFS('S9'!$I$6:$I$15,'S9'!$B$6:$B$15,$A84,'S9'!$E$6:$E$15,"Diego")+SUMIFS('S9'!$I$6:$I$15,'S9'!$B$6:$B$15,$A84,'S9'!$E$6:$E$15,"Ambos")+SUMIFS('S10'!$I$6:$I$13,'S10'!$B$6:$B$13,$A84,'S10'!$E$6:$E$13,"Diego")+SUMIFS('S10'!$I$6:$I$13,'S10'!$B$6:$B$13,$A84,'S10'!$E$6:$E$13,"Ambos")+SUMIFS('Holgura'!$I$6:$I$11,'Holgura'!$B$6:$B$11,$A84,'Holgura'!$E$6:$E$11,"Diego")+SUMIFS('Holgura'!$I$6:$I$11,'Holgura'!$B$6:$B$11,$A84,'Holgura'!$E$6:$E$11,"Ambos")+SUMIFS('Entrega'!$I$6:$I$9,'Entrega'!$B$6:$B$9,$A84,'Entrega'!$E$6:$E$9,"Diego")+SUMIFS('Entrega'!$I$6:$I$9,'Entrega'!$B$6:$B$9,$A84,'Entrega'!$E$6:$E$9,"Ambos")+SUMIFS('Defensa'!$I$6:$I$10,'Defensa'!$B$6:$B$10,$A84,'Defensa'!$E$6:$E$10,"Diego")+SUMIFS('Defensa'!$I$6:$I$10,'Defensa'!$B$6:$B$10,$A84,'Defensa'!$E$6:$E$10,"Ambos")</f>
+        <f>SUMIFS('S1'!$I$6:$I$32,'S1'!$B$6:$B$32,$A84,'S1'!$E$6:$E$32,"Diego")+SUMIFS('S1'!$I$6:$I$32,'S1'!$B$6:$B$32,$A84,'S1'!$E$6:$E$32,"Ambos")+SUMIFS('S2'!$I$6:$I$23,'S2'!$B$6:$B$23,$A84,'S2'!$E$6:$E$23,"Diego")+SUMIFS('S2'!$I$6:$I$23,'S2'!$B$6:$B$23,$A84,'S2'!$E$6:$E$23,"Ambos")+SUMIFS('S3'!$I$6:$I$24,'S3'!$B$6:$B$24,$A84,'S3'!$E$6:$E$24,"Diego")+SUMIFS('S3'!$I$6:$I$24,'S3'!$B$6:$B$24,$A84,'S3'!$E$6:$E$24,"Ambos")+SUMIFS('S4'!$I$6:$I$22,'S4'!$B$6:$B$22,$A84,'S4'!$E$6:$E$22,"Diego")+SUMIFS('S4'!$I$6:$I$22,'S4'!$B$6:$B$22,$A84,'S4'!$E$6:$E$22,"Ambos")+SUMIFS('S5'!$I$6:$I$20,'S5'!$B$6:$B$20,$A84,'S5'!$E$6:$E$20,"Diego")+SUMIFS('S5'!$I$6:$I$20,'S5'!$B$6:$B$20,$A84,'S5'!$E$6:$E$20,"Ambos")+SUMIFS('S6'!$I$6:$I$17,'S6'!$B$6:$B$17,$A84,'S6'!$E$6:$E$17,"Diego")+SUMIFS('S6'!$I$6:$I$17,'S6'!$B$6:$B$17,$A84,'S6'!$E$6:$E$17,"Ambos")+SUMIFS('S7'!$I$6:$I$19,'S7'!$B$6:$B$19,$A84,'S7'!$E$6:$E$19,"Diego")+SUMIFS('S7'!$I$6:$I$19,'S7'!$B$6:$B$19,$A84,'S7'!$E$6:$E$19,"Ambos")+SUMIFS('S8'!$I$6:$I$23,'S8'!$B$6:$B$23,$A84,'S8'!$E$6:$E$23,"Diego")+SUMIFS('S8'!$I$6:$I$23,'S8'!$B$6:$B$23,$A84,'S8'!$E$6:$E$23,"Ambos")+SUMIFS('S9'!$I$6:$I$15,'S9'!$B$6:$B$15,$A84,'S9'!$E$6:$E$15,"Diego")+SUMIFS('S9'!$I$6:$I$15,'S9'!$B$6:$B$15,$A84,'S9'!$E$6:$E$15,"Ambos")+SUMIFS('S10'!$I$6:$I$13,'S10'!$B$6:$B$13,$A84,'S10'!$E$6:$E$13,"Diego")+SUMIFS('S10'!$I$6:$I$13,'S10'!$B$6:$B$13,$A84,'S10'!$E$6:$E$13,"Ambos")+SUMIFS('Holgura'!$I$6:$I$11,'Holgura'!$B$6:$B$11,$A84,'Holgura'!$E$6:$E$11,"Diego")+SUMIFS('Holgura'!$I$6:$I$11,'Holgura'!$B$6:$B$11,$A84,'Holgura'!$E$6:$E$11,"Ambos")+SUMIFS('Entrega'!$I$6:$I$9,'Entrega'!$B$6:$B$9,$A84,'Entrega'!$E$6:$E$9,"Diego")+SUMIFS('Entrega'!$I$6:$I$9,'Entrega'!$B$6:$B$9,$A84,'Entrega'!$E$6:$E$9,"Ambos")+SUMIFS('Defensa'!$I$6:$I$10,'Defensa'!$B$6:$B$10,$A84,'Defensa'!$E$6:$E$10,"Diego")+SUMIFS('Defensa'!$I$6:$I$10,'Defensa'!$B$6:$B$10,$A84,'Defensa'!$E$6:$E$10,"Ambos")</f>
         <v/>
       </c>
       <c r="F84" s="21">
-        <f>COUNTIFS('S1'!$B$6:$B$32,$A84,'S1'!$E$6:$E$32,"Víctor")+COUNTIFS('S1'!$B$6:$B$32,$A84,'S1'!$E$6:$E$32,"Ambos")+COUNTIFS('S2'!$B$6:$B$23,$A84,'S2'!$E$6:$E$23,"Víctor")+COUNTIFS('S2'!$B$6:$B$23,$A84,'S2'!$E$6:$E$23,"Ambos")+COUNTIFS('S3'!$B$6:$B$19,$A84,'S3'!$E$6:$E$19,"Víctor")+COUNTIFS('S3'!$B$6:$B$19,$A84,'S3'!$E$6:$E$19,"Ambos")+COUNTIFS('S4'!$B$6:$B$20,$A84,'S4'!$E$6:$E$20,"Víctor")+COUNTIFS('S4'!$B$6:$B$20,$A84,'S4'!$E$6:$E$20,"Ambos")+COUNTIFS('S5'!$B$6:$B$20,$A84,'S5'!$E$6:$E$20,"Víctor")+COUNTIFS('S5'!$B$6:$B$20,$A84,'S5'!$E$6:$E$20,"Ambos")+COUNTIFS('S6'!$B$6:$B$17,$A84,'S6'!$E$6:$E$17,"Víctor")+COUNTIFS('S6'!$B$6:$B$17,$A84,'S6'!$E$6:$E$17,"Ambos")+COUNTIFS('S7'!$B$6:$B$19,$A84,'S7'!$E$6:$E$19,"Víctor")+COUNTIFS('S7'!$B$6:$B$19,$A84,'S7'!$E$6:$E$19,"Ambos")+COUNTIFS('S8'!$B$6:$B$23,$A84,'S8'!$E$6:$E$23,"Víctor")+COUNTIFS('S8'!$B$6:$B$23,$A84,'S8'!$E$6:$E$23,"Ambos")+COUNTIFS('S9'!$B$6:$B$15,$A84,'S9'!$E$6:$E$15,"Víctor")+COUNTIFS('S9'!$B$6:$B$15,$A84,'S9'!$E$6:$E$15,"Ambos")+COUNTIFS('S10'!$B$6:$B$13,$A84,'S10'!$E$6:$E$13,"Víctor")+COUNTIFS('S10'!$B$6:$B$13,$A84,'S10'!$E$6:$E$13,"Ambos")+COUNTIFS('Holgura'!$B$6:$B$11,$A84,'Holgura'!$E$6:$E$11,"Víctor")+COUNTIFS('Holgura'!$B$6:$B$11,$A84,'Holgura'!$E$6:$E$11,"Ambos")+COUNTIFS('Entrega'!$B$6:$B$9,$A84,'Entrega'!$E$6:$E$9,"Víctor")+COUNTIFS('Entrega'!$B$6:$B$9,$A84,'Entrega'!$E$6:$E$9,"Ambos")+COUNTIFS('Defensa'!$B$6:$B$10,$A84,'Defensa'!$E$6:$E$10,"Víctor")+COUNTIFS('Defensa'!$B$6:$B$10,$A84,'Defensa'!$E$6:$E$10,"Ambos")</f>
+        <f>COUNTIFS('S1'!$B$6:$B$32,$A84,'S1'!$E$6:$E$32,"Víctor")+COUNTIFS('S1'!$B$6:$B$32,$A84,'S1'!$E$6:$E$32,"Ambos")+COUNTIFS('S2'!$B$6:$B$23,$A84,'S2'!$E$6:$E$23,"Víctor")+COUNTIFS('S2'!$B$6:$B$23,$A84,'S2'!$E$6:$E$23,"Ambos")+COUNTIFS('S3'!$B$6:$B$24,$A84,'S3'!$E$6:$E$24,"Víctor")+COUNTIFS('S3'!$B$6:$B$24,$A84,'S3'!$E$6:$E$24,"Ambos")+COUNTIFS('S4'!$B$6:$B$22,$A84,'S4'!$E$6:$E$22,"Víctor")+COUNTIFS('S4'!$B$6:$B$22,$A84,'S4'!$E$6:$E$22,"Ambos")+COUNTIFS('S5'!$B$6:$B$20,$A84,'S5'!$E$6:$E$20,"Víctor")+COUNTIFS('S5'!$B$6:$B$20,$A84,'S5'!$E$6:$E$20,"Ambos")+COUNTIFS('S6'!$B$6:$B$17,$A84,'S6'!$E$6:$E$17,"Víctor")+COUNTIFS('S6'!$B$6:$B$17,$A84,'S6'!$E$6:$E$17,"Ambos")+COUNTIFS('S7'!$B$6:$B$19,$A84,'S7'!$E$6:$E$19,"Víctor")+COUNTIFS('S7'!$B$6:$B$19,$A84,'S7'!$E$6:$E$19,"Ambos")+COUNTIFS('S8'!$B$6:$B$23,$A84,'S8'!$E$6:$E$23,"Víctor")+COUNTIFS('S8'!$B$6:$B$23,$A84,'S8'!$E$6:$E$23,"Ambos")+COUNTIFS('S9'!$B$6:$B$15,$A84,'S9'!$E$6:$E$15,"Víctor")+COUNTIFS('S9'!$B$6:$B$15,$A84,'S9'!$E$6:$E$15,"Ambos")+COUNTIFS('S10'!$B$6:$B$13,$A84,'S10'!$E$6:$E$13,"Víctor")+COUNTIFS('S10'!$B$6:$B$13,$A84,'S10'!$E$6:$E$13,"Ambos")+COUNTIFS('Holgura'!$B$6:$B$11,$A84,'Holgura'!$E$6:$E$11,"Víctor")+COUNTIFS('Holgura'!$B$6:$B$11,$A84,'Holgura'!$E$6:$E$11,"Ambos")+COUNTIFS('Entrega'!$B$6:$B$9,$A84,'Entrega'!$E$6:$E$9,"Víctor")+COUNTIFS('Entrega'!$B$6:$B$9,$A84,'Entrega'!$E$6:$E$9,"Ambos")+COUNTIFS('Defensa'!$B$6:$B$10,$A84,'Defensa'!$E$6:$E$10,"Víctor")+COUNTIFS('Defensa'!$B$6:$B$10,$A84,'Defensa'!$E$6:$E$10,"Ambos")</f>
         <v/>
       </c>
       <c r="G84" s="21">
-        <f>COUNTIFS('S1'!$B$6:$B$32,$A84,'S1'!$E$6:$E$32,"Diego")+COUNTIFS('S1'!$B$6:$B$32,$A84,'S1'!$E$6:$E$32,"Ambos")+COUNTIFS('S2'!$B$6:$B$23,$A84,'S2'!$E$6:$E$23,"Diego")+COUNTIFS('S2'!$B$6:$B$23,$A84,'S2'!$E$6:$E$23,"Ambos")+COUNTIFS('S3'!$B$6:$B$19,$A84,'S3'!$E$6:$E$19,"Diego")+COUNTIFS('S3'!$B$6:$B$19,$A84,'S3'!$E$6:$E$19,"Ambos")+COUNTIFS('S4'!$B$6:$B$20,$A84,'S4'!$E$6:$E$20,"Diego")+COUNTIFS('S4'!$B$6:$B$20,$A84,'S4'!$E$6:$E$20,"Ambos")+COUNTIFS('S5'!$B$6:$B$20,$A84,'S5'!$E$6:$E$20,"Diego")+COUNTIFS('S5'!$B$6:$B$20,$A84,'S5'!$E$6:$E$20,"Ambos")+COUNTIFS('S6'!$B$6:$B$17,$A84,'S6'!$E$6:$E$17,"Diego")+COUNTIFS('S6'!$B$6:$B$17,$A84,'S6'!$E$6:$E$17,"Ambos")+COUNTIFS('S7'!$B$6:$B$19,$A84,'S7'!$E$6:$E$19,"Diego")+COUNTIFS('S7'!$B$6:$B$19,$A84,'S7'!$E$6:$E$19,"Ambos")+COUNTIFS('S8'!$B$6:$B$23,$A84,'S8'!$E$6:$E$23,"Diego")+COUNTIFS('S8'!$B$6:$B$23,$A84,'S8'!$E$6:$E$23,"Ambos")+COUNTIFS('S9'!$B$6:$B$15,$A84,'S9'!$E$6:$E$15,"Diego")+COUNTIFS('S9'!$B$6:$B$15,$A84,'S9'!$E$6:$E$15,"Ambos")+COUNTIFS('S10'!$B$6:$B$13,$A84,'S10'!$E$6:$E$13,"Diego")+COUNTIFS('S10'!$B$6:$B$13,$A84,'S10'!$E$6:$E$13,"Ambos")+COUNTIFS('Holgura'!$B$6:$B$11,$A84,'Holgura'!$E$6:$E$11,"Diego")+COUNTIFS('Holgura'!$B$6:$B$11,$A84,'Holgura'!$E$6:$E$11,"Ambos")+COUNTIFS('Entrega'!$B$6:$B$9,$A84,'Entrega'!$E$6:$E$9,"Diego")+COUNTIFS('Entrega'!$B$6:$B$9,$A84,'Entrega'!$E$6:$E$9,"Ambos")+COUNTIFS('Defensa'!$B$6:$B$10,$A84,'Defensa'!$E$6:$E$10,"Diego")+COUNTIFS('Defensa'!$B$6:$B$10,$A84,'Defensa'!$E$6:$E$10,"Ambos")</f>
+        <f>COUNTIFS('S1'!$B$6:$B$32,$A84,'S1'!$E$6:$E$32,"Diego")+COUNTIFS('S1'!$B$6:$B$32,$A84,'S1'!$E$6:$E$32,"Ambos")+COUNTIFS('S2'!$B$6:$B$23,$A84,'S2'!$E$6:$E$23,"Diego")+COUNTIFS('S2'!$B$6:$B$23,$A84,'S2'!$E$6:$E$23,"Ambos")+COUNTIFS('S3'!$B$6:$B$24,$A84,'S3'!$E$6:$E$24,"Diego")+COUNTIFS('S3'!$B$6:$B$24,$A84,'S3'!$E$6:$E$24,"Ambos")+COUNTIFS('S4'!$B$6:$B$22,$A84,'S4'!$E$6:$E$22,"Diego")+COUNTIFS('S4'!$B$6:$B$22,$A84,'S4'!$E$6:$E$22,"Ambos")+COUNTIFS('S5'!$B$6:$B$20,$A84,'S5'!$E$6:$E$20,"Diego")+COUNTIFS('S5'!$B$6:$B$20,$A84,'S5'!$E$6:$E$20,"Ambos")+COUNTIFS('S6'!$B$6:$B$17,$A84,'S6'!$E$6:$E$17,"Diego")+COUNTIFS('S6'!$B$6:$B$17,$A84,'S6'!$E$6:$E$17,"Ambos")+COUNTIFS('S7'!$B$6:$B$19,$A84,'S7'!$E$6:$E$19,"Diego")+COUNTIFS('S7'!$B$6:$B$19,$A84,'S7'!$E$6:$E$19,"Ambos")+COUNTIFS('S8'!$B$6:$B$23,$A84,'S8'!$E$6:$E$23,"Diego")+COUNTIFS('S8'!$B$6:$B$23,$A84,'S8'!$E$6:$E$23,"Ambos")+COUNTIFS('S9'!$B$6:$B$15,$A84,'S9'!$E$6:$E$15,"Diego")+COUNTIFS('S9'!$B$6:$B$15,$A84,'S9'!$E$6:$E$15,"Ambos")+COUNTIFS('S10'!$B$6:$B$13,$A84,'S10'!$E$6:$E$13,"Diego")+COUNTIFS('S10'!$B$6:$B$13,$A84,'S10'!$E$6:$E$13,"Ambos")+COUNTIFS('Holgura'!$B$6:$B$11,$A84,'Holgura'!$E$6:$E$11,"Diego")+COUNTIFS('Holgura'!$B$6:$B$11,$A84,'Holgura'!$E$6:$E$11,"Ambos")+COUNTIFS('Entrega'!$B$6:$B$9,$A84,'Entrega'!$E$6:$E$9,"Diego")+COUNTIFS('Entrega'!$B$6:$B$9,$A84,'Entrega'!$E$6:$E$9,"Ambos")+COUNTIFS('Defensa'!$B$6:$B$10,$A84,'Defensa'!$E$6:$E$10,"Diego")+COUNTIFS('Defensa'!$B$6:$B$10,$A84,'Defensa'!$E$6:$E$10,"Ambos")</f>
         <v/>
       </c>
     </row>
@@ -11000,19 +11021,19 @@
         <v/>
       </c>
       <c r="D85" s="21">
-        <f>SUMIFS('S1'!$I$6:$I$32,'S1'!$B$6:$B$32,$A85,'S1'!$E$6:$E$32,"Víctor")+SUMIFS('S1'!$I$6:$I$32,'S1'!$B$6:$B$32,$A85,'S1'!$E$6:$E$32,"Ambos")+SUMIFS('S2'!$I$6:$I$23,'S2'!$B$6:$B$23,$A85,'S2'!$E$6:$E$23,"Víctor")+SUMIFS('S2'!$I$6:$I$23,'S2'!$B$6:$B$23,$A85,'S2'!$E$6:$E$23,"Ambos")+SUMIFS('S3'!$I$6:$I$19,'S3'!$B$6:$B$19,$A85,'S3'!$E$6:$E$19,"Víctor")+SUMIFS('S3'!$I$6:$I$19,'S3'!$B$6:$B$19,$A85,'S3'!$E$6:$E$19,"Ambos")+SUMIFS('S4'!$I$6:$I$20,'S4'!$B$6:$B$20,$A85,'S4'!$E$6:$E$20,"Víctor")+SUMIFS('S4'!$I$6:$I$20,'S4'!$B$6:$B$20,$A85,'S4'!$E$6:$E$20,"Ambos")+SUMIFS('S5'!$I$6:$I$20,'S5'!$B$6:$B$20,$A85,'S5'!$E$6:$E$20,"Víctor")+SUMIFS('S5'!$I$6:$I$20,'S5'!$B$6:$B$20,$A85,'S5'!$E$6:$E$20,"Ambos")+SUMIFS('S6'!$I$6:$I$17,'S6'!$B$6:$B$17,$A85,'S6'!$E$6:$E$17,"Víctor")+SUMIFS('S6'!$I$6:$I$17,'S6'!$B$6:$B$17,$A85,'S6'!$E$6:$E$17,"Ambos")+SUMIFS('S7'!$I$6:$I$19,'S7'!$B$6:$B$19,$A85,'S7'!$E$6:$E$19,"Víctor")+SUMIFS('S7'!$I$6:$I$19,'S7'!$B$6:$B$19,$A85,'S7'!$E$6:$E$19,"Ambos")+SUMIFS('S8'!$I$6:$I$23,'S8'!$B$6:$B$23,$A85,'S8'!$E$6:$E$23,"Víctor")+SUMIFS('S8'!$I$6:$I$23,'S8'!$B$6:$B$23,$A85,'S8'!$E$6:$E$23,"Ambos")+SUMIFS('S9'!$I$6:$I$15,'S9'!$B$6:$B$15,$A85,'S9'!$E$6:$E$15,"Víctor")+SUMIFS('S9'!$I$6:$I$15,'S9'!$B$6:$B$15,$A85,'S9'!$E$6:$E$15,"Ambos")+SUMIFS('S10'!$I$6:$I$13,'S10'!$B$6:$B$13,$A85,'S10'!$E$6:$E$13,"Víctor")+SUMIFS('S10'!$I$6:$I$13,'S10'!$B$6:$B$13,$A85,'S10'!$E$6:$E$13,"Ambos")+SUMIFS('Holgura'!$I$6:$I$11,'Holgura'!$B$6:$B$11,$A85,'Holgura'!$E$6:$E$11,"Víctor")+SUMIFS('Holgura'!$I$6:$I$11,'Holgura'!$B$6:$B$11,$A85,'Holgura'!$E$6:$E$11,"Ambos")+SUMIFS('Entrega'!$I$6:$I$9,'Entrega'!$B$6:$B$9,$A85,'Entrega'!$E$6:$E$9,"Víctor")+SUMIFS('Entrega'!$I$6:$I$9,'Entrega'!$B$6:$B$9,$A85,'Entrega'!$E$6:$E$9,"Ambos")+SUMIFS('Defensa'!$I$6:$I$10,'Defensa'!$B$6:$B$10,$A85,'Defensa'!$E$6:$E$10,"Víctor")+SUMIFS('Defensa'!$I$6:$I$10,'Defensa'!$B$6:$B$10,$A85,'Defensa'!$E$6:$E$10,"Ambos")</f>
+        <f>SUMIFS('S1'!$I$6:$I$32,'S1'!$B$6:$B$32,$A85,'S1'!$E$6:$E$32,"Víctor")+SUMIFS('S1'!$I$6:$I$32,'S1'!$B$6:$B$32,$A85,'S1'!$E$6:$E$32,"Ambos")+SUMIFS('S2'!$I$6:$I$23,'S2'!$B$6:$B$23,$A85,'S2'!$E$6:$E$23,"Víctor")+SUMIFS('S2'!$I$6:$I$23,'S2'!$B$6:$B$23,$A85,'S2'!$E$6:$E$23,"Ambos")+SUMIFS('S3'!$I$6:$I$24,'S3'!$B$6:$B$24,$A85,'S3'!$E$6:$E$24,"Víctor")+SUMIFS('S3'!$I$6:$I$24,'S3'!$B$6:$B$24,$A85,'S3'!$E$6:$E$24,"Ambos")+SUMIFS('S4'!$I$6:$I$22,'S4'!$B$6:$B$22,$A85,'S4'!$E$6:$E$22,"Víctor")+SUMIFS('S4'!$I$6:$I$22,'S4'!$B$6:$B$22,$A85,'S4'!$E$6:$E$22,"Ambos")+SUMIFS('S5'!$I$6:$I$20,'S5'!$B$6:$B$20,$A85,'S5'!$E$6:$E$20,"Víctor")+SUMIFS('S5'!$I$6:$I$20,'S5'!$B$6:$B$20,$A85,'S5'!$E$6:$E$20,"Ambos")+SUMIFS('S6'!$I$6:$I$17,'S6'!$B$6:$B$17,$A85,'S6'!$E$6:$E$17,"Víctor")+SUMIFS('S6'!$I$6:$I$17,'S6'!$B$6:$B$17,$A85,'S6'!$E$6:$E$17,"Ambos")+SUMIFS('S7'!$I$6:$I$19,'S7'!$B$6:$B$19,$A85,'S7'!$E$6:$E$19,"Víctor")+SUMIFS('S7'!$I$6:$I$19,'S7'!$B$6:$B$19,$A85,'S7'!$E$6:$E$19,"Ambos")+SUMIFS('S8'!$I$6:$I$23,'S8'!$B$6:$B$23,$A85,'S8'!$E$6:$E$23,"Víctor")+SUMIFS('S8'!$I$6:$I$23,'S8'!$B$6:$B$23,$A85,'S8'!$E$6:$E$23,"Ambos")+SUMIFS('S9'!$I$6:$I$15,'S9'!$B$6:$B$15,$A85,'S9'!$E$6:$E$15,"Víctor")+SUMIFS('S9'!$I$6:$I$15,'S9'!$B$6:$B$15,$A85,'S9'!$E$6:$E$15,"Ambos")+SUMIFS('S10'!$I$6:$I$13,'S10'!$B$6:$B$13,$A85,'S10'!$E$6:$E$13,"Víctor")+SUMIFS('S10'!$I$6:$I$13,'S10'!$B$6:$B$13,$A85,'S10'!$E$6:$E$13,"Ambos")+SUMIFS('Holgura'!$I$6:$I$11,'Holgura'!$B$6:$B$11,$A85,'Holgura'!$E$6:$E$11,"Víctor")+SUMIFS('Holgura'!$I$6:$I$11,'Holgura'!$B$6:$B$11,$A85,'Holgura'!$E$6:$E$11,"Ambos")+SUMIFS('Entrega'!$I$6:$I$9,'Entrega'!$B$6:$B$9,$A85,'Entrega'!$E$6:$E$9,"Víctor")+SUMIFS('Entrega'!$I$6:$I$9,'Entrega'!$B$6:$B$9,$A85,'Entrega'!$E$6:$E$9,"Ambos")+SUMIFS('Defensa'!$I$6:$I$10,'Defensa'!$B$6:$B$10,$A85,'Defensa'!$E$6:$E$10,"Víctor")+SUMIFS('Defensa'!$I$6:$I$10,'Defensa'!$B$6:$B$10,$A85,'Defensa'!$E$6:$E$10,"Ambos")</f>
         <v/>
       </c>
       <c r="E85" s="21">
-        <f>SUMIFS('S1'!$I$6:$I$32,'S1'!$B$6:$B$32,$A85,'S1'!$E$6:$E$32,"Diego")+SUMIFS('S1'!$I$6:$I$32,'S1'!$B$6:$B$32,$A85,'S1'!$E$6:$E$32,"Ambos")+SUMIFS('S2'!$I$6:$I$23,'S2'!$B$6:$B$23,$A85,'S2'!$E$6:$E$23,"Diego")+SUMIFS('S2'!$I$6:$I$23,'S2'!$B$6:$B$23,$A85,'S2'!$E$6:$E$23,"Ambos")+SUMIFS('S3'!$I$6:$I$19,'S3'!$B$6:$B$19,$A85,'S3'!$E$6:$E$19,"Diego")+SUMIFS('S3'!$I$6:$I$19,'S3'!$B$6:$B$19,$A85,'S3'!$E$6:$E$19,"Ambos")+SUMIFS('S4'!$I$6:$I$20,'S4'!$B$6:$B$20,$A85,'S4'!$E$6:$E$20,"Diego")+SUMIFS('S4'!$I$6:$I$20,'S4'!$B$6:$B$20,$A85,'S4'!$E$6:$E$20,"Ambos")+SUMIFS('S5'!$I$6:$I$20,'S5'!$B$6:$B$20,$A85,'S5'!$E$6:$E$20,"Diego")+SUMIFS('S5'!$I$6:$I$20,'S5'!$B$6:$B$20,$A85,'S5'!$E$6:$E$20,"Ambos")+SUMIFS('S6'!$I$6:$I$17,'S6'!$B$6:$B$17,$A85,'S6'!$E$6:$E$17,"Diego")+SUMIFS('S6'!$I$6:$I$17,'S6'!$B$6:$B$17,$A85,'S6'!$E$6:$E$17,"Ambos")+SUMIFS('S7'!$I$6:$I$19,'S7'!$B$6:$B$19,$A85,'S7'!$E$6:$E$19,"Diego")+SUMIFS('S7'!$I$6:$I$19,'S7'!$B$6:$B$19,$A85,'S7'!$E$6:$E$19,"Ambos")+SUMIFS('S8'!$I$6:$I$23,'S8'!$B$6:$B$23,$A85,'S8'!$E$6:$E$23,"Diego")+SUMIFS('S8'!$I$6:$I$23,'S8'!$B$6:$B$23,$A85,'S8'!$E$6:$E$23,"Ambos")+SUMIFS('S9'!$I$6:$I$15,'S9'!$B$6:$B$15,$A85,'S9'!$E$6:$E$15,"Diego")+SUMIFS('S9'!$I$6:$I$15,'S9'!$B$6:$B$15,$A85,'S9'!$E$6:$E$15,"Ambos")+SUMIFS('S10'!$I$6:$I$13,'S10'!$B$6:$B$13,$A85,'S10'!$E$6:$E$13,"Diego")+SUMIFS('S10'!$I$6:$I$13,'S10'!$B$6:$B$13,$A85,'S10'!$E$6:$E$13,"Ambos")+SUMIFS('Holgura'!$I$6:$I$11,'Holgura'!$B$6:$B$11,$A85,'Holgura'!$E$6:$E$11,"Diego")+SUMIFS('Holgura'!$I$6:$I$11,'Holgura'!$B$6:$B$11,$A85,'Holgura'!$E$6:$E$11,"Ambos")+SUMIFS('Entrega'!$I$6:$I$9,'Entrega'!$B$6:$B$9,$A85,'Entrega'!$E$6:$E$9,"Diego")+SUMIFS('Entrega'!$I$6:$I$9,'Entrega'!$B$6:$B$9,$A85,'Entrega'!$E$6:$E$9,"Ambos")+SUMIFS('Defensa'!$I$6:$I$10,'Defensa'!$B$6:$B$10,$A85,'Defensa'!$E$6:$E$10,"Diego")+SUMIFS('Defensa'!$I$6:$I$10,'Defensa'!$B$6:$B$10,$A85,'Defensa'!$E$6:$E$10,"Ambos")</f>
+        <f>SUMIFS('S1'!$I$6:$I$32,'S1'!$B$6:$B$32,$A85,'S1'!$E$6:$E$32,"Diego")+SUMIFS('S1'!$I$6:$I$32,'S1'!$B$6:$B$32,$A85,'S1'!$E$6:$E$32,"Ambos")+SUMIFS('S2'!$I$6:$I$23,'S2'!$B$6:$B$23,$A85,'S2'!$E$6:$E$23,"Diego")+SUMIFS('S2'!$I$6:$I$23,'S2'!$B$6:$B$23,$A85,'S2'!$E$6:$E$23,"Ambos")+SUMIFS('S3'!$I$6:$I$24,'S3'!$B$6:$B$24,$A85,'S3'!$E$6:$E$24,"Diego")+SUMIFS('S3'!$I$6:$I$24,'S3'!$B$6:$B$24,$A85,'S3'!$E$6:$E$24,"Ambos")+SUMIFS('S4'!$I$6:$I$22,'S4'!$B$6:$B$22,$A85,'S4'!$E$6:$E$22,"Diego")+SUMIFS('S4'!$I$6:$I$22,'S4'!$B$6:$B$22,$A85,'S4'!$E$6:$E$22,"Ambos")+SUMIFS('S5'!$I$6:$I$20,'S5'!$B$6:$B$20,$A85,'S5'!$E$6:$E$20,"Diego")+SUMIFS('S5'!$I$6:$I$20,'S5'!$B$6:$B$20,$A85,'S5'!$E$6:$E$20,"Ambos")+SUMIFS('S6'!$I$6:$I$17,'S6'!$B$6:$B$17,$A85,'S6'!$E$6:$E$17,"Diego")+SUMIFS('S6'!$I$6:$I$17,'S6'!$B$6:$B$17,$A85,'S6'!$E$6:$E$17,"Ambos")+SUMIFS('S7'!$I$6:$I$19,'S7'!$B$6:$B$19,$A85,'S7'!$E$6:$E$19,"Diego")+SUMIFS('S7'!$I$6:$I$19,'S7'!$B$6:$B$19,$A85,'S7'!$E$6:$E$19,"Ambos")+SUMIFS('S8'!$I$6:$I$23,'S8'!$B$6:$B$23,$A85,'S8'!$E$6:$E$23,"Diego")+SUMIFS('S8'!$I$6:$I$23,'S8'!$B$6:$B$23,$A85,'S8'!$E$6:$E$23,"Ambos")+SUMIFS('S9'!$I$6:$I$15,'S9'!$B$6:$B$15,$A85,'S9'!$E$6:$E$15,"Diego")+SUMIFS('S9'!$I$6:$I$15,'S9'!$B$6:$B$15,$A85,'S9'!$E$6:$E$15,"Ambos")+SUMIFS('S10'!$I$6:$I$13,'S10'!$B$6:$B$13,$A85,'S10'!$E$6:$E$13,"Diego")+SUMIFS('S10'!$I$6:$I$13,'S10'!$B$6:$B$13,$A85,'S10'!$E$6:$E$13,"Ambos")+SUMIFS('Holgura'!$I$6:$I$11,'Holgura'!$B$6:$B$11,$A85,'Holgura'!$E$6:$E$11,"Diego")+SUMIFS('Holgura'!$I$6:$I$11,'Holgura'!$B$6:$B$11,$A85,'Holgura'!$E$6:$E$11,"Ambos")+SUMIFS('Entrega'!$I$6:$I$9,'Entrega'!$B$6:$B$9,$A85,'Entrega'!$E$6:$E$9,"Diego")+SUMIFS('Entrega'!$I$6:$I$9,'Entrega'!$B$6:$B$9,$A85,'Entrega'!$E$6:$E$9,"Ambos")+SUMIFS('Defensa'!$I$6:$I$10,'Defensa'!$B$6:$B$10,$A85,'Defensa'!$E$6:$E$10,"Diego")+SUMIFS('Defensa'!$I$6:$I$10,'Defensa'!$B$6:$B$10,$A85,'Defensa'!$E$6:$E$10,"Ambos")</f>
         <v/>
       </c>
       <c r="F85" s="21">
-        <f>COUNTIFS('S1'!$B$6:$B$32,$A85,'S1'!$E$6:$E$32,"Víctor")+COUNTIFS('S1'!$B$6:$B$32,$A85,'S1'!$E$6:$E$32,"Ambos")+COUNTIFS('S2'!$B$6:$B$23,$A85,'S2'!$E$6:$E$23,"Víctor")+COUNTIFS('S2'!$B$6:$B$23,$A85,'S2'!$E$6:$E$23,"Ambos")+COUNTIFS('S3'!$B$6:$B$19,$A85,'S3'!$E$6:$E$19,"Víctor")+COUNTIFS('S3'!$B$6:$B$19,$A85,'S3'!$E$6:$E$19,"Ambos")+COUNTIFS('S4'!$B$6:$B$20,$A85,'S4'!$E$6:$E$20,"Víctor")+COUNTIFS('S4'!$B$6:$B$20,$A85,'S4'!$E$6:$E$20,"Ambos")+COUNTIFS('S5'!$B$6:$B$20,$A85,'S5'!$E$6:$E$20,"Víctor")+COUNTIFS('S5'!$B$6:$B$20,$A85,'S5'!$E$6:$E$20,"Ambos")+COUNTIFS('S6'!$B$6:$B$17,$A85,'S6'!$E$6:$E$17,"Víctor")+COUNTIFS('S6'!$B$6:$B$17,$A85,'S6'!$E$6:$E$17,"Ambos")+COUNTIFS('S7'!$B$6:$B$19,$A85,'S7'!$E$6:$E$19,"Víctor")+COUNTIFS('S7'!$B$6:$B$19,$A85,'S7'!$E$6:$E$19,"Ambos")+COUNTIFS('S8'!$B$6:$B$23,$A85,'S8'!$E$6:$E$23,"Víctor")+COUNTIFS('S8'!$B$6:$B$23,$A85,'S8'!$E$6:$E$23,"Ambos")+COUNTIFS('S9'!$B$6:$B$15,$A85,'S9'!$E$6:$E$15,"Víctor")+COUNTIFS('S9'!$B$6:$B$15,$A85,'S9'!$E$6:$E$15,"Ambos")+COUNTIFS('S10'!$B$6:$B$13,$A85,'S10'!$E$6:$E$13,"Víctor")+COUNTIFS('S10'!$B$6:$B$13,$A85,'S10'!$E$6:$E$13,"Ambos")+COUNTIFS('Holgura'!$B$6:$B$11,$A85,'Holgura'!$E$6:$E$11,"Víctor")+COUNTIFS('Holgura'!$B$6:$B$11,$A85,'Holgura'!$E$6:$E$11,"Ambos")+COUNTIFS('Entrega'!$B$6:$B$9,$A85,'Entrega'!$E$6:$E$9,"Víctor")+COUNTIFS('Entrega'!$B$6:$B$9,$A85,'Entrega'!$E$6:$E$9,"Ambos")+COUNTIFS('Defensa'!$B$6:$B$10,$A85,'Defensa'!$E$6:$E$10,"Víctor")+COUNTIFS('Defensa'!$B$6:$B$10,$A85,'Defensa'!$E$6:$E$10,"Ambos")</f>
+        <f>COUNTIFS('S1'!$B$6:$B$32,$A85,'S1'!$E$6:$E$32,"Víctor")+COUNTIFS('S1'!$B$6:$B$32,$A85,'S1'!$E$6:$E$32,"Ambos")+COUNTIFS('S2'!$B$6:$B$23,$A85,'S2'!$E$6:$E$23,"Víctor")+COUNTIFS('S2'!$B$6:$B$23,$A85,'S2'!$E$6:$E$23,"Ambos")+COUNTIFS('S3'!$B$6:$B$24,$A85,'S3'!$E$6:$E$24,"Víctor")+COUNTIFS('S3'!$B$6:$B$24,$A85,'S3'!$E$6:$E$24,"Ambos")+COUNTIFS('S4'!$B$6:$B$22,$A85,'S4'!$E$6:$E$22,"Víctor")+COUNTIFS('S4'!$B$6:$B$22,$A85,'S4'!$E$6:$E$22,"Ambos")+COUNTIFS('S5'!$B$6:$B$20,$A85,'S5'!$E$6:$E$20,"Víctor")+COUNTIFS('S5'!$B$6:$B$20,$A85,'S5'!$E$6:$E$20,"Ambos")+COUNTIFS('S6'!$B$6:$B$17,$A85,'S6'!$E$6:$E$17,"Víctor")+COUNTIFS('S6'!$B$6:$B$17,$A85,'S6'!$E$6:$E$17,"Ambos")+COUNTIFS('S7'!$B$6:$B$19,$A85,'S7'!$E$6:$E$19,"Víctor")+COUNTIFS('S7'!$B$6:$B$19,$A85,'S7'!$E$6:$E$19,"Ambos")+COUNTIFS('S8'!$B$6:$B$23,$A85,'S8'!$E$6:$E$23,"Víctor")+COUNTIFS('S8'!$B$6:$B$23,$A85,'S8'!$E$6:$E$23,"Ambos")+COUNTIFS('S9'!$B$6:$B$15,$A85,'S9'!$E$6:$E$15,"Víctor")+COUNTIFS('S9'!$B$6:$B$15,$A85,'S9'!$E$6:$E$15,"Ambos")+COUNTIFS('S10'!$B$6:$B$13,$A85,'S10'!$E$6:$E$13,"Víctor")+COUNTIFS('S10'!$B$6:$B$13,$A85,'S10'!$E$6:$E$13,"Ambos")+COUNTIFS('Holgura'!$B$6:$B$11,$A85,'Holgura'!$E$6:$E$11,"Víctor")+COUNTIFS('Holgura'!$B$6:$B$11,$A85,'Holgura'!$E$6:$E$11,"Ambos")+COUNTIFS('Entrega'!$B$6:$B$9,$A85,'Entrega'!$E$6:$E$9,"Víctor")+COUNTIFS('Entrega'!$B$6:$B$9,$A85,'Entrega'!$E$6:$E$9,"Ambos")+COUNTIFS('Defensa'!$B$6:$B$10,$A85,'Defensa'!$E$6:$E$10,"Víctor")+COUNTIFS('Defensa'!$B$6:$B$10,$A85,'Defensa'!$E$6:$E$10,"Ambos")</f>
         <v/>
       </c>
       <c r="G85" s="21">
-        <f>COUNTIFS('S1'!$B$6:$B$32,$A85,'S1'!$E$6:$E$32,"Diego")+COUNTIFS('S1'!$B$6:$B$32,$A85,'S1'!$E$6:$E$32,"Ambos")+COUNTIFS('S2'!$B$6:$B$23,$A85,'S2'!$E$6:$E$23,"Diego")+COUNTIFS('S2'!$B$6:$B$23,$A85,'S2'!$E$6:$E$23,"Ambos")+COUNTIFS('S3'!$B$6:$B$19,$A85,'S3'!$E$6:$E$19,"Diego")+COUNTIFS('S3'!$B$6:$B$19,$A85,'S3'!$E$6:$E$19,"Ambos")+COUNTIFS('S4'!$B$6:$B$20,$A85,'S4'!$E$6:$E$20,"Diego")+COUNTIFS('S4'!$B$6:$B$20,$A85,'S4'!$E$6:$E$20,"Ambos")+COUNTIFS('S5'!$B$6:$B$20,$A85,'S5'!$E$6:$E$20,"Diego")+COUNTIFS('S5'!$B$6:$B$20,$A85,'S5'!$E$6:$E$20,"Ambos")+COUNTIFS('S6'!$B$6:$B$17,$A85,'S6'!$E$6:$E$17,"Diego")+COUNTIFS('S6'!$B$6:$B$17,$A85,'S6'!$E$6:$E$17,"Ambos")+COUNTIFS('S7'!$B$6:$B$19,$A85,'S7'!$E$6:$E$19,"Diego")+COUNTIFS('S7'!$B$6:$B$19,$A85,'S7'!$E$6:$E$19,"Ambos")+COUNTIFS('S8'!$B$6:$B$23,$A85,'S8'!$E$6:$E$23,"Diego")+COUNTIFS('S8'!$B$6:$B$23,$A85,'S8'!$E$6:$E$23,"Ambos")+COUNTIFS('S9'!$B$6:$B$15,$A85,'S9'!$E$6:$E$15,"Diego")+COUNTIFS('S9'!$B$6:$B$15,$A85,'S9'!$E$6:$E$15,"Ambos")+COUNTIFS('S10'!$B$6:$B$13,$A85,'S10'!$E$6:$E$13,"Diego")+COUNTIFS('S10'!$B$6:$B$13,$A85,'S10'!$E$6:$E$13,"Ambos")+COUNTIFS('Holgura'!$B$6:$B$11,$A85,'Holgura'!$E$6:$E$11,"Diego")+COUNTIFS('Holgura'!$B$6:$B$11,$A85,'Holgura'!$E$6:$E$11,"Ambos")+COUNTIFS('Entrega'!$B$6:$B$9,$A85,'Entrega'!$E$6:$E$9,"Diego")+COUNTIFS('Entrega'!$B$6:$B$9,$A85,'Entrega'!$E$6:$E$9,"Ambos")+COUNTIFS('Defensa'!$B$6:$B$10,$A85,'Defensa'!$E$6:$E$10,"Diego")+COUNTIFS('Defensa'!$B$6:$B$10,$A85,'Defensa'!$E$6:$E$10,"Ambos")</f>
+        <f>COUNTIFS('S1'!$B$6:$B$32,$A85,'S1'!$E$6:$E$32,"Diego")+COUNTIFS('S1'!$B$6:$B$32,$A85,'S1'!$E$6:$E$32,"Ambos")+COUNTIFS('S2'!$B$6:$B$23,$A85,'S2'!$E$6:$E$23,"Diego")+COUNTIFS('S2'!$B$6:$B$23,$A85,'S2'!$E$6:$E$23,"Ambos")+COUNTIFS('S3'!$B$6:$B$24,$A85,'S3'!$E$6:$E$24,"Diego")+COUNTIFS('S3'!$B$6:$B$24,$A85,'S3'!$E$6:$E$24,"Ambos")+COUNTIFS('S4'!$B$6:$B$22,$A85,'S4'!$E$6:$E$22,"Diego")+COUNTIFS('S4'!$B$6:$B$22,$A85,'S4'!$E$6:$E$22,"Ambos")+COUNTIFS('S5'!$B$6:$B$20,$A85,'S5'!$E$6:$E$20,"Diego")+COUNTIFS('S5'!$B$6:$B$20,$A85,'S5'!$E$6:$E$20,"Ambos")+COUNTIFS('S6'!$B$6:$B$17,$A85,'S6'!$E$6:$E$17,"Diego")+COUNTIFS('S6'!$B$6:$B$17,$A85,'S6'!$E$6:$E$17,"Ambos")+COUNTIFS('S7'!$B$6:$B$19,$A85,'S7'!$E$6:$E$19,"Diego")+COUNTIFS('S7'!$B$6:$B$19,$A85,'S7'!$E$6:$E$19,"Ambos")+COUNTIFS('S8'!$B$6:$B$23,$A85,'S8'!$E$6:$E$23,"Diego")+COUNTIFS('S8'!$B$6:$B$23,$A85,'S8'!$E$6:$E$23,"Ambos")+COUNTIFS('S9'!$B$6:$B$15,$A85,'S9'!$E$6:$E$15,"Diego")+COUNTIFS('S9'!$B$6:$B$15,$A85,'S9'!$E$6:$E$15,"Ambos")+COUNTIFS('S10'!$B$6:$B$13,$A85,'S10'!$E$6:$E$13,"Diego")+COUNTIFS('S10'!$B$6:$B$13,$A85,'S10'!$E$6:$E$13,"Ambos")+COUNTIFS('Holgura'!$B$6:$B$11,$A85,'Holgura'!$E$6:$E$11,"Diego")+COUNTIFS('Holgura'!$B$6:$B$11,$A85,'Holgura'!$E$6:$E$11,"Ambos")+COUNTIFS('Entrega'!$B$6:$B$9,$A85,'Entrega'!$E$6:$E$9,"Diego")+COUNTIFS('Entrega'!$B$6:$B$9,$A85,'Entrega'!$E$6:$E$9,"Ambos")+COUNTIFS('Defensa'!$B$6:$B$10,$A85,'Defensa'!$E$6:$E$10,"Diego")+COUNTIFS('Defensa'!$B$6:$B$10,$A85,'Defensa'!$E$6:$E$10,"Ambos")</f>
         <v/>
       </c>
     </row>
@@ -11029,19 +11050,19 @@
         <v/>
       </c>
       <c r="D86" s="21">
-        <f>SUMIFS('S1'!$I$6:$I$32,'S1'!$B$6:$B$32,$A86,'S1'!$E$6:$E$32,"Víctor")+SUMIFS('S1'!$I$6:$I$32,'S1'!$B$6:$B$32,$A86,'S1'!$E$6:$E$32,"Ambos")+SUMIFS('S2'!$I$6:$I$23,'S2'!$B$6:$B$23,$A86,'S2'!$E$6:$E$23,"Víctor")+SUMIFS('S2'!$I$6:$I$23,'S2'!$B$6:$B$23,$A86,'S2'!$E$6:$E$23,"Ambos")+SUMIFS('S3'!$I$6:$I$19,'S3'!$B$6:$B$19,$A86,'S3'!$E$6:$E$19,"Víctor")+SUMIFS('S3'!$I$6:$I$19,'S3'!$B$6:$B$19,$A86,'S3'!$E$6:$E$19,"Ambos")+SUMIFS('S4'!$I$6:$I$20,'S4'!$B$6:$B$20,$A86,'S4'!$E$6:$E$20,"Víctor")+SUMIFS('S4'!$I$6:$I$20,'S4'!$B$6:$B$20,$A86,'S4'!$E$6:$E$20,"Ambos")+SUMIFS('S5'!$I$6:$I$20,'S5'!$B$6:$B$20,$A86,'S5'!$E$6:$E$20,"Víctor")+SUMIFS('S5'!$I$6:$I$20,'S5'!$B$6:$B$20,$A86,'S5'!$E$6:$E$20,"Ambos")+SUMIFS('S6'!$I$6:$I$17,'S6'!$B$6:$B$17,$A86,'S6'!$E$6:$E$17,"Víctor")+SUMIFS('S6'!$I$6:$I$17,'S6'!$B$6:$B$17,$A86,'S6'!$E$6:$E$17,"Ambos")+SUMIFS('S7'!$I$6:$I$19,'S7'!$B$6:$B$19,$A86,'S7'!$E$6:$E$19,"Víctor")+SUMIFS('S7'!$I$6:$I$19,'S7'!$B$6:$B$19,$A86,'S7'!$E$6:$E$19,"Ambos")+SUMIFS('S8'!$I$6:$I$23,'S8'!$B$6:$B$23,$A86,'S8'!$E$6:$E$23,"Víctor")+SUMIFS('S8'!$I$6:$I$23,'S8'!$B$6:$B$23,$A86,'S8'!$E$6:$E$23,"Ambos")+SUMIFS('S9'!$I$6:$I$15,'S9'!$B$6:$B$15,$A86,'S9'!$E$6:$E$15,"Víctor")+SUMIFS('S9'!$I$6:$I$15,'S9'!$B$6:$B$15,$A86,'S9'!$E$6:$E$15,"Ambos")+SUMIFS('S10'!$I$6:$I$13,'S10'!$B$6:$B$13,$A86,'S10'!$E$6:$E$13,"Víctor")+SUMIFS('S10'!$I$6:$I$13,'S10'!$B$6:$B$13,$A86,'S10'!$E$6:$E$13,"Ambos")+SUMIFS('Holgura'!$I$6:$I$11,'Holgura'!$B$6:$B$11,$A86,'Holgura'!$E$6:$E$11,"Víctor")+SUMIFS('Holgura'!$I$6:$I$11,'Holgura'!$B$6:$B$11,$A86,'Holgura'!$E$6:$E$11,"Ambos")+SUMIFS('Entrega'!$I$6:$I$9,'Entrega'!$B$6:$B$9,$A86,'Entrega'!$E$6:$E$9,"Víctor")+SUMIFS('Entrega'!$I$6:$I$9,'Entrega'!$B$6:$B$9,$A86,'Entrega'!$E$6:$E$9,"Ambos")+SUMIFS('Defensa'!$I$6:$I$10,'Defensa'!$B$6:$B$10,$A86,'Defensa'!$E$6:$E$10,"Víctor")+SUMIFS('Defensa'!$I$6:$I$10,'Defensa'!$B$6:$B$10,$A86,'Defensa'!$E$6:$E$10,"Ambos")</f>
+        <f>SUMIFS('S1'!$I$6:$I$32,'S1'!$B$6:$B$32,$A86,'S1'!$E$6:$E$32,"Víctor")+SUMIFS('S1'!$I$6:$I$32,'S1'!$B$6:$B$32,$A86,'S1'!$E$6:$E$32,"Ambos")+SUMIFS('S2'!$I$6:$I$23,'S2'!$B$6:$B$23,$A86,'S2'!$E$6:$E$23,"Víctor")+SUMIFS('S2'!$I$6:$I$23,'S2'!$B$6:$B$23,$A86,'S2'!$E$6:$E$23,"Ambos")+SUMIFS('S3'!$I$6:$I$24,'S3'!$B$6:$B$24,$A86,'S3'!$E$6:$E$24,"Víctor")+SUMIFS('S3'!$I$6:$I$24,'S3'!$B$6:$B$24,$A86,'S3'!$E$6:$E$24,"Ambos")+SUMIFS('S4'!$I$6:$I$22,'S4'!$B$6:$B$22,$A86,'S4'!$E$6:$E$22,"Víctor")+SUMIFS('S4'!$I$6:$I$22,'S4'!$B$6:$B$22,$A86,'S4'!$E$6:$E$22,"Ambos")+SUMIFS('S5'!$I$6:$I$20,'S5'!$B$6:$B$20,$A86,'S5'!$E$6:$E$20,"Víctor")+SUMIFS('S5'!$I$6:$I$20,'S5'!$B$6:$B$20,$A86,'S5'!$E$6:$E$20,"Ambos")+SUMIFS('S6'!$I$6:$I$17,'S6'!$B$6:$B$17,$A86,'S6'!$E$6:$E$17,"Víctor")+SUMIFS('S6'!$I$6:$I$17,'S6'!$B$6:$B$17,$A86,'S6'!$E$6:$E$17,"Ambos")+SUMIFS('S7'!$I$6:$I$19,'S7'!$B$6:$B$19,$A86,'S7'!$E$6:$E$19,"Víctor")+SUMIFS('S7'!$I$6:$I$19,'S7'!$B$6:$B$19,$A86,'S7'!$E$6:$E$19,"Ambos")+SUMIFS('S8'!$I$6:$I$23,'S8'!$B$6:$B$23,$A86,'S8'!$E$6:$E$23,"Víctor")+SUMIFS('S8'!$I$6:$I$23,'S8'!$B$6:$B$23,$A86,'S8'!$E$6:$E$23,"Ambos")+SUMIFS('S9'!$I$6:$I$15,'S9'!$B$6:$B$15,$A86,'S9'!$E$6:$E$15,"Víctor")+SUMIFS('S9'!$I$6:$I$15,'S9'!$B$6:$B$15,$A86,'S9'!$E$6:$E$15,"Ambos")+SUMIFS('S10'!$I$6:$I$13,'S10'!$B$6:$B$13,$A86,'S10'!$E$6:$E$13,"Víctor")+SUMIFS('S10'!$I$6:$I$13,'S10'!$B$6:$B$13,$A86,'S10'!$E$6:$E$13,"Ambos")+SUMIFS('Holgura'!$I$6:$I$11,'Holgura'!$B$6:$B$11,$A86,'Holgura'!$E$6:$E$11,"Víctor")+SUMIFS('Holgura'!$I$6:$I$11,'Holgura'!$B$6:$B$11,$A86,'Holgura'!$E$6:$E$11,"Ambos")+SUMIFS('Entrega'!$I$6:$I$9,'Entrega'!$B$6:$B$9,$A86,'Entrega'!$E$6:$E$9,"Víctor")+SUMIFS('Entrega'!$I$6:$I$9,'Entrega'!$B$6:$B$9,$A86,'Entrega'!$E$6:$E$9,"Ambos")+SUMIFS('Defensa'!$I$6:$I$10,'Defensa'!$B$6:$B$10,$A86,'Defensa'!$E$6:$E$10,"Víctor")+SUMIFS('Defensa'!$I$6:$I$10,'Defensa'!$B$6:$B$10,$A86,'Defensa'!$E$6:$E$10,"Ambos")</f>
         <v/>
       </c>
       <c r="E86" s="21">
-        <f>SUMIFS('S1'!$I$6:$I$32,'S1'!$B$6:$B$32,$A86,'S1'!$E$6:$E$32,"Diego")+SUMIFS('S1'!$I$6:$I$32,'S1'!$B$6:$B$32,$A86,'S1'!$E$6:$E$32,"Ambos")+SUMIFS('S2'!$I$6:$I$23,'S2'!$B$6:$B$23,$A86,'S2'!$E$6:$E$23,"Diego")+SUMIFS('S2'!$I$6:$I$23,'S2'!$B$6:$B$23,$A86,'S2'!$E$6:$E$23,"Ambos")+SUMIFS('S3'!$I$6:$I$19,'S3'!$B$6:$B$19,$A86,'S3'!$E$6:$E$19,"Diego")+SUMIFS('S3'!$I$6:$I$19,'S3'!$B$6:$B$19,$A86,'S3'!$E$6:$E$19,"Ambos")+SUMIFS('S4'!$I$6:$I$20,'S4'!$B$6:$B$20,$A86,'S4'!$E$6:$E$20,"Diego")+SUMIFS('S4'!$I$6:$I$20,'S4'!$B$6:$B$20,$A86,'S4'!$E$6:$E$20,"Ambos")+SUMIFS('S5'!$I$6:$I$20,'S5'!$B$6:$B$20,$A86,'S5'!$E$6:$E$20,"Diego")+SUMIFS('S5'!$I$6:$I$20,'S5'!$B$6:$B$20,$A86,'S5'!$E$6:$E$20,"Ambos")+SUMIFS('S6'!$I$6:$I$17,'S6'!$B$6:$B$17,$A86,'S6'!$E$6:$E$17,"Diego")+SUMIFS('S6'!$I$6:$I$17,'S6'!$B$6:$B$17,$A86,'S6'!$E$6:$E$17,"Ambos")+SUMIFS('S7'!$I$6:$I$19,'S7'!$B$6:$B$19,$A86,'S7'!$E$6:$E$19,"Diego")+SUMIFS('S7'!$I$6:$I$19,'S7'!$B$6:$B$19,$A86,'S7'!$E$6:$E$19,"Ambos")+SUMIFS('S8'!$I$6:$I$23,'S8'!$B$6:$B$23,$A86,'S8'!$E$6:$E$23,"Diego")+SUMIFS('S8'!$I$6:$I$23,'S8'!$B$6:$B$23,$A86,'S8'!$E$6:$E$23,"Ambos")+SUMIFS('S9'!$I$6:$I$15,'S9'!$B$6:$B$15,$A86,'S9'!$E$6:$E$15,"Diego")+SUMIFS('S9'!$I$6:$I$15,'S9'!$B$6:$B$15,$A86,'S9'!$E$6:$E$15,"Ambos")+SUMIFS('S10'!$I$6:$I$13,'S10'!$B$6:$B$13,$A86,'S10'!$E$6:$E$13,"Diego")+SUMIFS('S10'!$I$6:$I$13,'S10'!$B$6:$B$13,$A86,'S10'!$E$6:$E$13,"Ambos")+SUMIFS('Holgura'!$I$6:$I$11,'Holgura'!$B$6:$B$11,$A86,'Holgura'!$E$6:$E$11,"Diego")+SUMIFS('Holgura'!$I$6:$I$11,'Holgura'!$B$6:$B$11,$A86,'Holgura'!$E$6:$E$11,"Ambos")+SUMIFS('Entrega'!$I$6:$I$9,'Entrega'!$B$6:$B$9,$A86,'Entrega'!$E$6:$E$9,"Diego")+SUMIFS('Entrega'!$I$6:$I$9,'Entrega'!$B$6:$B$9,$A86,'Entrega'!$E$6:$E$9,"Ambos")+SUMIFS('Defensa'!$I$6:$I$10,'Defensa'!$B$6:$B$10,$A86,'Defensa'!$E$6:$E$10,"Diego")+SUMIFS('Defensa'!$I$6:$I$10,'Defensa'!$B$6:$B$10,$A86,'Defensa'!$E$6:$E$10,"Ambos")</f>
+        <f>SUMIFS('S1'!$I$6:$I$32,'S1'!$B$6:$B$32,$A86,'S1'!$E$6:$E$32,"Diego")+SUMIFS('S1'!$I$6:$I$32,'S1'!$B$6:$B$32,$A86,'S1'!$E$6:$E$32,"Ambos")+SUMIFS('S2'!$I$6:$I$23,'S2'!$B$6:$B$23,$A86,'S2'!$E$6:$E$23,"Diego")+SUMIFS('S2'!$I$6:$I$23,'S2'!$B$6:$B$23,$A86,'S2'!$E$6:$E$23,"Ambos")+SUMIFS('S3'!$I$6:$I$24,'S3'!$B$6:$B$24,$A86,'S3'!$E$6:$E$24,"Diego")+SUMIFS('S3'!$I$6:$I$24,'S3'!$B$6:$B$24,$A86,'S3'!$E$6:$E$24,"Ambos")+SUMIFS('S4'!$I$6:$I$22,'S4'!$B$6:$B$22,$A86,'S4'!$E$6:$E$22,"Diego")+SUMIFS('S4'!$I$6:$I$22,'S4'!$B$6:$B$22,$A86,'S4'!$E$6:$E$22,"Ambos")+SUMIFS('S5'!$I$6:$I$20,'S5'!$B$6:$B$20,$A86,'S5'!$E$6:$E$20,"Diego")+SUMIFS('S5'!$I$6:$I$20,'S5'!$B$6:$B$20,$A86,'S5'!$E$6:$E$20,"Ambos")+SUMIFS('S6'!$I$6:$I$17,'S6'!$B$6:$B$17,$A86,'S6'!$E$6:$E$17,"Diego")+SUMIFS('S6'!$I$6:$I$17,'S6'!$B$6:$B$17,$A86,'S6'!$E$6:$E$17,"Ambos")+SUMIFS('S7'!$I$6:$I$19,'S7'!$B$6:$B$19,$A86,'S7'!$E$6:$E$19,"Diego")+SUMIFS('S7'!$I$6:$I$19,'S7'!$B$6:$B$19,$A86,'S7'!$E$6:$E$19,"Ambos")+SUMIFS('S8'!$I$6:$I$23,'S8'!$B$6:$B$23,$A86,'S8'!$E$6:$E$23,"Diego")+SUMIFS('S8'!$I$6:$I$23,'S8'!$B$6:$B$23,$A86,'S8'!$E$6:$E$23,"Ambos")+SUMIFS('S9'!$I$6:$I$15,'S9'!$B$6:$B$15,$A86,'S9'!$E$6:$E$15,"Diego")+SUMIFS('S9'!$I$6:$I$15,'S9'!$B$6:$B$15,$A86,'S9'!$E$6:$E$15,"Ambos")+SUMIFS('S10'!$I$6:$I$13,'S10'!$B$6:$B$13,$A86,'S10'!$E$6:$E$13,"Diego")+SUMIFS('S10'!$I$6:$I$13,'S10'!$B$6:$B$13,$A86,'S10'!$E$6:$E$13,"Ambos")+SUMIFS('Holgura'!$I$6:$I$11,'Holgura'!$B$6:$B$11,$A86,'Holgura'!$E$6:$E$11,"Diego")+SUMIFS('Holgura'!$I$6:$I$11,'Holgura'!$B$6:$B$11,$A86,'Holgura'!$E$6:$E$11,"Ambos")+SUMIFS('Entrega'!$I$6:$I$9,'Entrega'!$B$6:$B$9,$A86,'Entrega'!$E$6:$E$9,"Diego")+SUMIFS('Entrega'!$I$6:$I$9,'Entrega'!$B$6:$B$9,$A86,'Entrega'!$E$6:$E$9,"Ambos")+SUMIFS('Defensa'!$I$6:$I$10,'Defensa'!$B$6:$B$10,$A86,'Defensa'!$E$6:$E$10,"Diego")+SUMIFS('Defensa'!$I$6:$I$10,'Defensa'!$B$6:$B$10,$A86,'Defensa'!$E$6:$E$10,"Ambos")</f>
         <v/>
       </c>
       <c r="F86" s="21">
-        <f>COUNTIFS('S1'!$B$6:$B$32,$A86,'S1'!$E$6:$E$32,"Víctor")+COUNTIFS('S1'!$B$6:$B$32,$A86,'S1'!$E$6:$E$32,"Ambos")+COUNTIFS('S2'!$B$6:$B$23,$A86,'S2'!$E$6:$E$23,"Víctor")+COUNTIFS('S2'!$B$6:$B$23,$A86,'S2'!$E$6:$E$23,"Ambos")+COUNTIFS('S3'!$B$6:$B$19,$A86,'S3'!$E$6:$E$19,"Víctor")+COUNTIFS('S3'!$B$6:$B$19,$A86,'S3'!$E$6:$E$19,"Ambos")+COUNTIFS('S4'!$B$6:$B$20,$A86,'S4'!$E$6:$E$20,"Víctor")+COUNTIFS('S4'!$B$6:$B$20,$A86,'S4'!$E$6:$E$20,"Ambos")+COUNTIFS('S5'!$B$6:$B$20,$A86,'S5'!$E$6:$E$20,"Víctor")+COUNTIFS('S5'!$B$6:$B$20,$A86,'S5'!$E$6:$E$20,"Ambos")+COUNTIFS('S6'!$B$6:$B$17,$A86,'S6'!$E$6:$E$17,"Víctor")+COUNTIFS('S6'!$B$6:$B$17,$A86,'S6'!$E$6:$E$17,"Ambos")+COUNTIFS('S7'!$B$6:$B$19,$A86,'S7'!$E$6:$E$19,"Víctor")+COUNTIFS('S7'!$B$6:$B$19,$A86,'S7'!$E$6:$E$19,"Ambos")+COUNTIFS('S8'!$B$6:$B$23,$A86,'S8'!$E$6:$E$23,"Víctor")+COUNTIFS('S8'!$B$6:$B$23,$A86,'S8'!$E$6:$E$23,"Ambos")+COUNTIFS('S9'!$B$6:$B$15,$A86,'S9'!$E$6:$E$15,"Víctor")+COUNTIFS('S9'!$B$6:$B$15,$A86,'S9'!$E$6:$E$15,"Ambos")+COUNTIFS('S10'!$B$6:$B$13,$A86,'S10'!$E$6:$E$13,"Víctor")+COUNTIFS('S10'!$B$6:$B$13,$A86,'S10'!$E$6:$E$13,"Ambos")+COUNTIFS('Holgura'!$B$6:$B$11,$A86,'Holgura'!$E$6:$E$11,"Víctor")+COUNTIFS('Holgura'!$B$6:$B$11,$A86,'Holgura'!$E$6:$E$11,"Ambos")+COUNTIFS('Entrega'!$B$6:$B$9,$A86,'Entrega'!$E$6:$E$9,"Víctor")+COUNTIFS('Entrega'!$B$6:$B$9,$A86,'Entrega'!$E$6:$E$9,"Ambos")+COUNTIFS('Defensa'!$B$6:$B$10,$A86,'Defensa'!$E$6:$E$10,"Víctor")+COUNTIFS('Defensa'!$B$6:$B$10,$A86,'Defensa'!$E$6:$E$10,"Ambos")</f>
+        <f>COUNTIFS('S1'!$B$6:$B$32,$A86,'S1'!$E$6:$E$32,"Víctor")+COUNTIFS('S1'!$B$6:$B$32,$A86,'S1'!$E$6:$E$32,"Ambos")+COUNTIFS('S2'!$B$6:$B$23,$A86,'S2'!$E$6:$E$23,"Víctor")+COUNTIFS('S2'!$B$6:$B$23,$A86,'S2'!$E$6:$E$23,"Ambos")+COUNTIFS('S3'!$B$6:$B$24,$A86,'S3'!$E$6:$E$24,"Víctor")+COUNTIFS('S3'!$B$6:$B$24,$A86,'S3'!$E$6:$E$24,"Ambos")+COUNTIFS('S4'!$B$6:$B$22,$A86,'S4'!$E$6:$E$22,"Víctor")+COUNTIFS('S4'!$B$6:$B$22,$A86,'S4'!$E$6:$E$22,"Ambos")+COUNTIFS('S5'!$B$6:$B$20,$A86,'S5'!$E$6:$E$20,"Víctor")+COUNTIFS('S5'!$B$6:$B$20,$A86,'S5'!$E$6:$E$20,"Ambos")+COUNTIFS('S6'!$B$6:$B$17,$A86,'S6'!$E$6:$E$17,"Víctor")+COUNTIFS('S6'!$B$6:$B$17,$A86,'S6'!$E$6:$E$17,"Ambos")+COUNTIFS('S7'!$B$6:$B$19,$A86,'S7'!$E$6:$E$19,"Víctor")+COUNTIFS('S7'!$B$6:$B$19,$A86,'S7'!$E$6:$E$19,"Ambos")+COUNTIFS('S8'!$B$6:$B$23,$A86,'S8'!$E$6:$E$23,"Víctor")+COUNTIFS('S8'!$B$6:$B$23,$A86,'S8'!$E$6:$E$23,"Ambos")+COUNTIFS('S9'!$B$6:$B$15,$A86,'S9'!$E$6:$E$15,"Víctor")+COUNTIFS('S9'!$B$6:$B$15,$A86,'S9'!$E$6:$E$15,"Ambos")+COUNTIFS('S10'!$B$6:$B$13,$A86,'S10'!$E$6:$E$13,"Víctor")+COUNTIFS('S10'!$B$6:$B$13,$A86,'S10'!$E$6:$E$13,"Ambos")+COUNTIFS('Holgura'!$B$6:$B$11,$A86,'Holgura'!$E$6:$E$11,"Víctor")+COUNTIFS('Holgura'!$B$6:$B$11,$A86,'Holgura'!$E$6:$E$11,"Ambos")+COUNTIFS('Entrega'!$B$6:$B$9,$A86,'Entrega'!$E$6:$E$9,"Víctor")+COUNTIFS('Entrega'!$B$6:$B$9,$A86,'Entrega'!$E$6:$E$9,"Ambos")+COUNTIFS('Defensa'!$B$6:$B$10,$A86,'Defensa'!$E$6:$E$10,"Víctor")+COUNTIFS('Defensa'!$B$6:$B$10,$A86,'Defensa'!$E$6:$E$10,"Ambos")</f>
         <v/>
       </c>
       <c r="G86" s="21">
-        <f>COUNTIFS('S1'!$B$6:$B$32,$A86,'S1'!$E$6:$E$32,"Diego")+COUNTIFS('S1'!$B$6:$B$32,$A86,'S1'!$E$6:$E$32,"Ambos")+COUNTIFS('S2'!$B$6:$B$23,$A86,'S2'!$E$6:$E$23,"Diego")+COUNTIFS('S2'!$B$6:$B$23,$A86,'S2'!$E$6:$E$23,"Ambos")+COUNTIFS('S3'!$B$6:$B$19,$A86,'S3'!$E$6:$E$19,"Diego")+COUNTIFS('S3'!$B$6:$B$19,$A86,'S3'!$E$6:$E$19,"Ambos")+COUNTIFS('S4'!$B$6:$B$20,$A86,'S4'!$E$6:$E$20,"Diego")+COUNTIFS('S4'!$B$6:$B$20,$A86,'S4'!$E$6:$E$20,"Ambos")+COUNTIFS('S5'!$B$6:$B$20,$A86,'S5'!$E$6:$E$20,"Diego")+COUNTIFS('S5'!$B$6:$B$20,$A86,'S5'!$E$6:$E$20,"Ambos")+COUNTIFS('S6'!$B$6:$B$17,$A86,'S6'!$E$6:$E$17,"Diego")+COUNTIFS('S6'!$B$6:$B$17,$A86,'S6'!$E$6:$E$17,"Ambos")+COUNTIFS('S7'!$B$6:$B$19,$A86,'S7'!$E$6:$E$19,"Diego")+COUNTIFS('S7'!$B$6:$B$19,$A86,'S7'!$E$6:$E$19,"Ambos")+COUNTIFS('S8'!$B$6:$B$23,$A86,'S8'!$E$6:$E$23,"Diego")+COUNTIFS('S8'!$B$6:$B$23,$A86,'S8'!$E$6:$E$23,"Ambos")+COUNTIFS('S9'!$B$6:$B$15,$A86,'S9'!$E$6:$E$15,"Diego")+COUNTIFS('S9'!$B$6:$B$15,$A86,'S9'!$E$6:$E$15,"Ambos")+COUNTIFS('S10'!$B$6:$B$13,$A86,'S10'!$E$6:$E$13,"Diego")+COUNTIFS('S10'!$B$6:$B$13,$A86,'S10'!$E$6:$E$13,"Ambos")+COUNTIFS('Holgura'!$B$6:$B$11,$A86,'Holgura'!$E$6:$E$11,"Diego")+COUNTIFS('Holgura'!$B$6:$B$11,$A86,'Holgura'!$E$6:$E$11,"Ambos")+COUNTIFS('Entrega'!$B$6:$B$9,$A86,'Entrega'!$E$6:$E$9,"Diego")+COUNTIFS('Entrega'!$B$6:$B$9,$A86,'Entrega'!$E$6:$E$9,"Ambos")+COUNTIFS('Defensa'!$B$6:$B$10,$A86,'Defensa'!$E$6:$E$10,"Diego")+COUNTIFS('Defensa'!$B$6:$B$10,$A86,'Defensa'!$E$6:$E$10,"Ambos")</f>
+        <f>COUNTIFS('S1'!$B$6:$B$32,$A86,'S1'!$E$6:$E$32,"Diego")+COUNTIFS('S1'!$B$6:$B$32,$A86,'S1'!$E$6:$E$32,"Ambos")+COUNTIFS('S2'!$B$6:$B$23,$A86,'S2'!$E$6:$E$23,"Diego")+COUNTIFS('S2'!$B$6:$B$23,$A86,'S2'!$E$6:$E$23,"Ambos")+COUNTIFS('S3'!$B$6:$B$24,$A86,'S3'!$E$6:$E$24,"Diego")+COUNTIFS('S3'!$B$6:$B$24,$A86,'S3'!$E$6:$E$24,"Ambos")+COUNTIFS('S4'!$B$6:$B$22,$A86,'S4'!$E$6:$E$22,"Diego")+COUNTIFS('S4'!$B$6:$B$22,$A86,'S4'!$E$6:$E$22,"Ambos")+COUNTIFS('S5'!$B$6:$B$20,$A86,'S5'!$E$6:$E$20,"Diego")+COUNTIFS('S5'!$B$6:$B$20,$A86,'S5'!$E$6:$E$20,"Ambos")+COUNTIFS('S6'!$B$6:$B$17,$A86,'S6'!$E$6:$E$17,"Diego")+COUNTIFS('S6'!$B$6:$B$17,$A86,'S6'!$E$6:$E$17,"Ambos")+COUNTIFS('S7'!$B$6:$B$19,$A86,'S7'!$E$6:$E$19,"Diego")+COUNTIFS('S7'!$B$6:$B$19,$A86,'S7'!$E$6:$E$19,"Ambos")+COUNTIFS('S8'!$B$6:$B$23,$A86,'S8'!$E$6:$E$23,"Diego")+COUNTIFS('S8'!$B$6:$B$23,$A86,'S8'!$E$6:$E$23,"Ambos")+COUNTIFS('S9'!$B$6:$B$15,$A86,'S9'!$E$6:$E$15,"Diego")+COUNTIFS('S9'!$B$6:$B$15,$A86,'S9'!$E$6:$E$15,"Ambos")+COUNTIFS('S10'!$B$6:$B$13,$A86,'S10'!$E$6:$E$13,"Diego")+COUNTIFS('S10'!$B$6:$B$13,$A86,'S10'!$E$6:$E$13,"Ambos")+COUNTIFS('Holgura'!$B$6:$B$11,$A86,'Holgura'!$E$6:$E$11,"Diego")+COUNTIFS('Holgura'!$B$6:$B$11,$A86,'Holgura'!$E$6:$E$11,"Ambos")+COUNTIFS('Entrega'!$B$6:$B$9,$A86,'Entrega'!$E$6:$E$9,"Diego")+COUNTIFS('Entrega'!$B$6:$B$9,$A86,'Entrega'!$E$6:$E$9,"Ambos")+COUNTIFS('Defensa'!$B$6:$B$10,$A86,'Defensa'!$E$6:$E$10,"Diego")+COUNTIFS('Defensa'!$B$6:$B$10,$A86,'Defensa'!$E$6:$E$10,"Ambos")</f>
         <v/>
       </c>
     </row>
@@ -11058,19 +11079,19 @@
         <v/>
       </c>
       <c r="D87" s="21">
-        <f>SUMIFS('S1'!$I$6:$I$32,'S1'!$B$6:$B$32,$A87,'S1'!$E$6:$E$32,"Víctor")+SUMIFS('S1'!$I$6:$I$32,'S1'!$B$6:$B$32,$A87,'S1'!$E$6:$E$32,"Ambos")+SUMIFS('S2'!$I$6:$I$23,'S2'!$B$6:$B$23,$A87,'S2'!$E$6:$E$23,"Víctor")+SUMIFS('S2'!$I$6:$I$23,'S2'!$B$6:$B$23,$A87,'S2'!$E$6:$E$23,"Ambos")+SUMIFS('S3'!$I$6:$I$19,'S3'!$B$6:$B$19,$A87,'S3'!$E$6:$E$19,"Víctor")+SUMIFS('S3'!$I$6:$I$19,'S3'!$B$6:$B$19,$A87,'S3'!$E$6:$E$19,"Ambos")+SUMIFS('S4'!$I$6:$I$20,'S4'!$B$6:$B$20,$A87,'S4'!$E$6:$E$20,"Víctor")+SUMIFS('S4'!$I$6:$I$20,'S4'!$B$6:$B$20,$A87,'S4'!$E$6:$E$20,"Ambos")+SUMIFS('S5'!$I$6:$I$20,'S5'!$B$6:$B$20,$A87,'S5'!$E$6:$E$20,"Víctor")+SUMIFS('S5'!$I$6:$I$20,'S5'!$B$6:$B$20,$A87,'S5'!$E$6:$E$20,"Ambos")+SUMIFS('S6'!$I$6:$I$17,'S6'!$B$6:$B$17,$A87,'S6'!$E$6:$E$17,"Víctor")+SUMIFS('S6'!$I$6:$I$17,'S6'!$B$6:$B$17,$A87,'S6'!$E$6:$E$17,"Ambos")+SUMIFS('S7'!$I$6:$I$19,'S7'!$B$6:$B$19,$A87,'S7'!$E$6:$E$19,"Víctor")+SUMIFS('S7'!$I$6:$I$19,'S7'!$B$6:$B$19,$A87,'S7'!$E$6:$E$19,"Ambos")+SUMIFS('S8'!$I$6:$I$23,'S8'!$B$6:$B$23,$A87,'S8'!$E$6:$E$23,"Víctor")+SUMIFS('S8'!$I$6:$I$23,'S8'!$B$6:$B$23,$A87,'S8'!$E$6:$E$23,"Ambos")+SUMIFS('S9'!$I$6:$I$15,'S9'!$B$6:$B$15,$A87,'S9'!$E$6:$E$15,"Víctor")+SUMIFS('S9'!$I$6:$I$15,'S9'!$B$6:$B$15,$A87,'S9'!$E$6:$E$15,"Ambos")+SUMIFS('S10'!$I$6:$I$13,'S10'!$B$6:$B$13,$A87,'S10'!$E$6:$E$13,"Víctor")+SUMIFS('S10'!$I$6:$I$13,'S10'!$B$6:$B$13,$A87,'S10'!$E$6:$E$13,"Ambos")+SUMIFS('Holgura'!$I$6:$I$11,'Holgura'!$B$6:$B$11,$A87,'Holgura'!$E$6:$E$11,"Víctor")+SUMIFS('Holgura'!$I$6:$I$11,'Holgura'!$B$6:$B$11,$A87,'Holgura'!$E$6:$E$11,"Ambos")+SUMIFS('Entrega'!$I$6:$I$9,'Entrega'!$B$6:$B$9,$A87,'Entrega'!$E$6:$E$9,"Víctor")+SUMIFS('Entrega'!$I$6:$I$9,'Entrega'!$B$6:$B$9,$A87,'Entrega'!$E$6:$E$9,"Ambos")+SUMIFS('Defensa'!$I$6:$I$10,'Defensa'!$B$6:$B$10,$A87,'Defensa'!$E$6:$E$10,"Víctor")+SUMIFS('Defensa'!$I$6:$I$10,'Defensa'!$B$6:$B$10,$A87,'Defensa'!$E$6:$E$10,"Ambos")</f>
+        <f>SUMIFS('S1'!$I$6:$I$32,'S1'!$B$6:$B$32,$A87,'S1'!$E$6:$E$32,"Víctor")+SUMIFS('S1'!$I$6:$I$32,'S1'!$B$6:$B$32,$A87,'S1'!$E$6:$E$32,"Ambos")+SUMIFS('S2'!$I$6:$I$23,'S2'!$B$6:$B$23,$A87,'S2'!$E$6:$E$23,"Víctor")+SUMIFS('S2'!$I$6:$I$23,'S2'!$B$6:$B$23,$A87,'S2'!$E$6:$E$23,"Ambos")+SUMIFS('S3'!$I$6:$I$24,'S3'!$B$6:$B$24,$A87,'S3'!$E$6:$E$24,"Víctor")+SUMIFS('S3'!$I$6:$I$24,'S3'!$B$6:$B$24,$A87,'S3'!$E$6:$E$24,"Ambos")+SUMIFS('S4'!$I$6:$I$22,'S4'!$B$6:$B$22,$A87,'S4'!$E$6:$E$22,"Víctor")+SUMIFS('S4'!$I$6:$I$22,'S4'!$B$6:$B$22,$A87,'S4'!$E$6:$E$22,"Ambos")+SUMIFS('S5'!$I$6:$I$20,'S5'!$B$6:$B$20,$A87,'S5'!$E$6:$E$20,"Víctor")+SUMIFS('S5'!$I$6:$I$20,'S5'!$B$6:$B$20,$A87,'S5'!$E$6:$E$20,"Ambos")+SUMIFS('S6'!$I$6:$I$17,'S6'!$B$6:$B$17,$A87,'S6'!$E$6:$E$17,"Víctor")+SUMIFS('S6'!$I$6:$I$17,'S6'!$B$6:$B$17,$A87,'S6'!$E$6:$E$17,"Ambos")+SUMIFS('S7'!$I$6:$I$19,'S7'!$B$6:$B$19,$A87,'S7'!$E$6:$E$19,"Víctor")+SUMIFS('S7'!$I$6:$I$19,'S7'!$B$6:$B$19,$A87,'S7'!$E$6:$E$19,"Ambos")+SUMIFS('S8'!$I$6:$I$23,'S8'!$B$6:$B$23,$A87,'S8'!$E$6:$E$23,"Víctor")+SUMIFS('S8'!$I$6:$I$23,'S8'!$B$6:$B$23,$A87,'S8'!$E$6:$E$23,"Ambos")+SUMIFS('S9'!$I$6:$I$15,'S9'!$B$6:$B$15,$A87,'S9'!$E$6:$E$15,"Víctor")+SUMIFS('S9'!$I$6:$I$15,'S9'!$B$6:$B$15,$A87,'S9'!$E$6:$E$15,"Ambos")+SUMIFS('S10'!$I$6:$I$13,'S10'!$B$6:$B$13,$A87,'S10'!$E$6:$E$13,"Víctor")+SUMIFS('S10'!$I$6:$I$13,'S10'!$B$6:$B$13,$A87,'S10'!$E$6:$E$13,"Ambos")+SUMIFS('Holgura'!$I$6:$I$11,'Holgura'!$B$6:$B$11,$A87,'Holgura'!$E$6:$E$11,"Víctor")+SUMIFS('Holgura'!$I$6:$I$11,'Holgura'!$B$6:$B$11,$A87,'Holgura'!$E$6:$E$11,"Ambos")+SUMIFS('Entrega'!$I$6:$I$9,'Entrega'!$B$6:$B$9,$A87,'Entrega'!$E$6:$E$9,"Víctor")+SUMIFS('Entrega'!$I$6:$I$9,'Entrega'!$B$6:$B$9,$A87,'Entrega'!$E$6:$E$9,"Ambos")+SUMIFS('Defensa'!$I$6:$I$10,'Defensa'!$B$6:$B$10,$A87,'Defensa'!$E$6:$E$10,"Víctor")+SUMIFS('Defensa'!$I$6:$I$10,'Defensa'!$B$6:$B$10,$A87,'Defensa'!$E$6:$E$10,"Ambos")</f>
         <v/>
       </c>
       <c r="E87" s="21">
-        <f>SUMIFS('S1'!$I$6:$I$32,'S1'!$B$6:$B$32,$A87,'S1'!$E$6:$E$32,"Diego")+SUMIFS('S1'!$I$6:$I$32,'S1'!$B$6:$B$32,$A87,'S1'!$E$6:$E$32,"Ambos")+SUMIFS('S2'!$I$6:$I$23,'S2'!$B$6:$B$23,$A87,'S2'!$E$6:$E$23,"Diego")+SUMIFS('S2'!$I$6:$I$23,'S2'!$B$6:$B$23,$A87,'S2'!$E$6:$E$23,"Ambos")+SUMIFS('S3'!$I$6:$I$19,'S3'!$B$6:$B$19,$A87,'S3'!$E$6:$E$19,"Diego")+SUMIFS('S3'!$I$6:$I$19,'S3'!$B$6:$B$19,$A87,'S3'!$E$6:$E$19,"Ambos")+SUMIFS('S4'!$I$6:$I$20,'S4'!$B$6:$B$20,$A87,'S4'!$E$6:$E$20,"Diego")+SUMIFS('S4'!$I$6:$I$20,'S4'!$B$6:$B$20,$A87,'S4'!$E$6:$E$20,"Ambos")+SUMIFS('S5'!$I$6:$I$20,'S5'!$B$6:$B$20,$A87,'S5'!$E$6:$E$20,"Diego")+SUMIFS('S5'!$I$6:$I$20,'S5'!$B$6:$B$20,$A87,'S5'!$E$6:$E$20,"Ambos")+SUMIFS('S6'!$I$6:$I$17,'S6'!$B$6:$B$17,$A87,'S6'!$E$6:$E$17,"Diego")+SUMIFS('S6'!$I$6:$I$17,'S6'!$B$6:$B$17,$A87,'S6'!$E$6:$E$17,"Ambos")+SUMIFS('S7'!$I$6:$I$19,'S7'!$B$6:$B$19,$A87,'S7'!$E$6:$E$19,"Diego")+SUMIFS('S7'!$I$6:$I$19,'S7'!$B$6:$B$19,$A87,'S7'!$E$6:$E$19,"Ambos")+SUMIFS('S8'!$I$6:$I$23,'S8'!$B$6:$B$23,$A87,'S8'!$E$6:$E$23,"Diego")+SUMIFS('S8'!$I$6:$I$23,'S8'!$B$6:$B$23,$A87,'S8'!$E$6:$E$23,"Ambos")+SUMIFS('S9'!$I$6:$I$15,'S9'!$B$6:$B$15,$A87,'S9'!$E$6:$E$15,"Diego")+SUMIFS('S9'!$I$6:$I$15,'S9'!$B$6:$B$15,$A87,'S9'!$E$6:$E$15,"Ambos")+SUMIFS('S10'!$I$6:$I$13,'S10'!$B$6:$B$13,$A87,'S10'!$E$6:$E$13,"Diego")+SUMIFS('S10'!$I$6:$I$13,'S10'!$B$6:$B$13,$A87,'S10'!$E$6:$E$13,"Ambos")+SUMIFS('Holgura'!$I$6:$I$11,'Holgura'!$B$6:$B$11,$A87,'Holgura'!$E$6:$E$11,"Diego")+SUMIFS('Holgura'!$I$6:$I$11,'Holgura'!$B$6:$B$11,$A87,'Holgura'!$E$6:$E$11,"Ambos")+SUMIFS('Entrega'!$I$6:$I$9,'Entrega'!$B$6:$B$9,$A87,'Entrega'!$E$6:$E$9,"Diego")+SUMIFS('Entrega'!$I$6:$I$9,'Entrega'!$B$6:$B$9,$A87,'Entrega'!$E$6:$E$9,"Ambos")+SUMIFS('Defensa'!$I$6:$I$10,'Defensa'!$B$6:$B$10,$A87,'Defensa'!$E$6:$E$10,"Diego")+SUMIFS('Defensa'!$I$6:$I$10,'Defensa'!$B$6:$B$10,$A87,'Defensa'!$E$6:$E$10,"Ambos")</f>
+        <f>SUMIFS('S1'!$I$6:$I$32,'S1'!$B$6:$B$32,$A87,'S1'!$E$6:$E$32,"Diego")+SUMIFS('S1'!$I$6:$I$32,'S1'!$B$6:$B$32,$A87,'S1'!$E$6:$E$32,"Ambos")+SUMIFS('S2'!$I$6:$I$23,'S2'!$B$6:$B$23,$A87,'S2'!$E$6:$E$23,"Diego")+SUMIFS('S2'!$I$6:$I$23,'S2'!$B$6:$B$23,$A87,'S2'!$E$6:$E$23,"Ambos")+SUMIFS('S3'!$I$6:$I$24,'S3'!$B$6:$B$24,$A87,'S3'!$E$6:$E$24,"Diego")+SUMIFS('S3'!$I$6:$I$24,'S3'!$B$6:$B$24,$A87,'S3'!$E$6:$E$24,"Ambos")+SUMIFS('S4'!$I$6:$I$22,'S4'!$B$6:$B$22,$A87,'S4'!$E$6:$E$22,"Diego")+SUMIFS('S4'!$I$6:$I$22,'S4'!$B$6:$B$22,$A87,'S4'!$E$6:$E$22,"Ambos")+SUMIFS('S5'!$I$6:$I$20,'S5'!$B$6:$B$20,$A87,'S5'!$E$6:$E$20,"Diego")+SUMIFS('S5'!$I$6:$I$20,'S5'!$B$6:$B$20,$A87,'S5'!$E$6:$E$20,"Ambos")+SUMIFS('S6'!$I$6:$I$17,'S6'!$B$6:$B$17,$A87,'S6'!$E$6:$E$17,"Diego")+SUMIFS('S6'!$I$6:$I$17,'S6'!$B$6:$B$17,$A87,'S6'!$E$6:$E$17,"Ambos")+SUMIFS('S7'!$I$6:$I$19,'S7'!$B$6:$B$19,$A87,'S7'!$E$6:$E$19,"Diego")+SUMIFS('S7'!$I$6:$I$19,'S7'!$B$6:$B$19,$A87,'S7'!$E$6:$E$19,"Ambos")+SUMIFS('S8'!$I$6:$I$23,'S8'!$B$6:$B$23,$A87,'S8'!$E$6:$E$23,"Diego")+SUMIFS('S8'!$I$6:$I$23,'S8'!$B$6:$B$23,$A87,'S8'!$E$6:$E$23,"Ambos")+SUMIFS('S9'!$I$6:$I$15,'S9'!$B$6:$B$15,$A87,'S9'!$E$6:$E$15,"Diego")+SUMIFS('S9'!$I$6:$I$15,'S9'!$B$6:$B$15,$A87,'S9'!$E$6:$E$15,"Ambos")+SUMIFS('S10'!$I$6:$I$13,'S10'!$B$6:$B$13,$A87,'S10'!$E$6:$E$13,"Diego")+SUMIFS('S10'!$I$6:$I$13,'S10'!$B$6:$B$13,$A87,'S10'!$E$6:$E$13,"Ambos")+SUMIFS('Holgura'!$I$6:$I$11,'Holgura'!$B$6:$B$11,$A87,'Holgura'!$E$6:$E$11,"Diego")+SUMIFS('Holgura'!$I$6:$I$11,'Holgura'!$B$6:$B$11,$A87,'Holgura'!$E$6:$E$11,"Ambos")+SUMIFS('Entrega'!$I$6:$I$9,'Entrega'!$B$6:$B$9,$A87,'Entrega'!$E$6:$E$9,"Diego")+SUMIFS('Entrega'!$I$6:$I$9,'Entrega'!$B$6:$B$9,$A87,'Entrega'!$E$6:$E$9,"Ambos")+SUMIFS('Defensa'!$I$6:$I$10,'Defensa'!$B$6:$B$10,$A87,'Defensa'!$E$6:$E$10,"Diego")+SUMIFS('Defensa'!$I$6:$I$10,'Defensa'!$B$6:$B$10,$A87,'Defensa'!$E$6:$E$10,"Ambos")</f>
         <v/>
       </c>
       <c r="F87" s="21">
-        <f>COUNTIFS('S1'!$B$6:$B$32,$A87,'S1'!$E$6:$E$32,"Víctor")+COUNTIFS('S1'!$B$6:$B$32,$A87,'S1'!$E$6:$E$32,"Ambos")+COUNTIFS('S2'!$B$6:$B$23,$A87,'S2'!$E$6:$E$23,"Víctor")+COUNTIFS('S2'!$B$6:$B$23,$A87,'S2'!$E$6:$E$23,"Ambos")+COUNTIFS('S3'!$B$6:$B$19,$A87,'S3'!$E$6:$E$19,"Víctor")+COUNTIFS('S3'!$B$6:$B$19,$A87,'S3'!$E$6:$E$19,"Ambos")+COUNTIFS('S4'!$B$6:$B$20,$A87,'S4'!$E$6:$E$20,"Víctor")+COUNTIFS('S4'!$B$6:$B$20,$A87,'S4'!$E$6:$E$20,"Ambos")+COUNTIFS('S5'!$B$6:$B$20,$A87,'S5'!$E$6:$E$20,"Víctor")+COUNTIFS('S5'!$B$6:$B$20,$A87,'S5'!$E$6:$E$20,"Ambos")+COUNTIFS('S6'!$B$6:$B$17,$A87,'S6'!$E$6:$E$17,"Víctor")+COUNTIFS('S6'!$B$6:$B$17,$A87,'S6'!$E$6:$E$17,"Ambos")+COUNTIFS('S7'!$B$6:$B$19,$A87,'S7'!$E$6:$E$19,"Víctor")+COUNTIFS('S7'!$B$6:$B$19,$A87,'S7'!$E$6:$E$19,"Ambos")+COUNTIFS('S8'!$B$6:$B$23,$A87,'S8'!$E$6:$E$23,"Víctor")+COUNTIFS('S8'!$B$6:$B$23,$A87,'S8'!$E$6:$E$23,"Ambos")+COUNTIFS('S9'!$B$6:$B$15,$A87,'S9'!$E$6:$E$15,"Víctor")+COUNTIFS('S9'!$B$6:$B$15,$A87,'S9'!$E$6:$E$15,"Ambos")+COUNTIFS('S10'!$B$6:$B$13,$A87,'S10'!$E$6:$E$13,"Víctor")+COUNTIFS('S10'!$B$6:$B$13,$A87,'S10'!$E$6:$E$13,"Ambos")+COUNTIFS('Holgura'!$B$6:$B$11,$A87,'Holgura'!$E$6:$E$11,"Víctor")+COUNTIFS('Holgura'!$B$6:$B$11,$A87,'Holgura'!$E$6:$E$11,"Ambos")+COUNTIFS('Entrega'!$B$6:$B$9,$A87,'Entrega'!$E$6:$E$9,"Víctor")+COUNTIFS('Entrega'!$B$6:$B$9,$A87,'Entrega'!$E$6:$E$9,"Ambos")+COUNTIFS('Defensa'!$B$6:$B$10,$A87,'Defensa'!$E$6:$E$10,"Víctor")+COUNTIFS('Defensa'!$B$6:$B$10,$A87,'Defensa'!$E$6:$E$10,"Ambos")</f>
+        <f>COUNTIFS('S1'!$B$6:$B$32,$A87,'S1'!$E$6:$E$32,"Víctor")+COUNTIFS('S1'!$B$6:$B$32,$A87,'S1'!$E$6:$E$32,"Ambos")+COUNTIFS('S2'!$B$6:$B$23,$A87,'S2'!$E$6:$E$23,"Víctor")+COUNTIFS('S2'!$B$6:$B$23,$A87,'S2'!$E$6:$E$23,"Ambos")+COUNTIFS('S3'!$B$6:$B$24,$A87,'S3'!$E$6:$E$24,"Víctor")+COUNTIFS('S3'!$B$6:$B$24,$A87,'S3'!$E$6:$E$24,"Ambos")+COUNTIFS('S4'!$B$6:$B$22,$A87,'S4'!$E$6:$E$22,"Víctor")+COUNTIFS('S4'!$B$6:$B$22,$A87,'S4'!$E$6:$E$22,"Ambos")+COUNTIFS('S5'!$B$6:$B$20,$A87,'S5'!$E$6:$E$20,"Víctor")+COUNTIFS('S5'!$B$6:$B$20,$A87,'S5'!$E$6:$E$20,"Ambos")+COUNTIFS('S6'!$B$6:$B$17,$A87,'S6'!$E$6:$E$17,"Víctor")+COUNTIFS('S6'!$B$6:$B$17,$A87,'S6'!$E$6:$E$17,"Ambos")+COUNTIFS('S7'!$B$6:$B$19,$A87,'S7'!$E$6:$E$19,"Víctor")+COUNTIFS('S7'!$B$6:$B$19,$A87,'S7'!$E$6:$E$19,"Ambos")+COUNTIFS('S8'!$B$6:$B$23,$A87,'S8'!$E$6:$E$23,"Víctor")+COUNTIFS('S8'!$B$6:$B$23,$A87,'S8'!$E$6:$E$23,"Ambos")+COUNTIFS('S9'!$B$6:$B$15,$A87,'S9'!$E$6:$E$15,"Víctor")+COUNTIFS('S9'!$B$6:$B$15,$A87,'S9'!$E$6:$E$15,"Ambos")+COUNTIFS('S10'!$B$6:$B$13,$A87,'S10'!$E$6:$E$13,"Víctor")+COUNTIFS('S10'!$B$6:$B$13,$A87,'S10'!$E$6:$E$13,"Ambos")+COUNTIFS('Holgura'!$B$6:$B$11,$A87,'Holgura'!$E$6:$E$11,"Víctor")+COUNTIFS('Holgura'!$B$6:$B$11,$A87,'Holgura'!$E$6:$E$11,"Ambos")+COUNTIFS('Entrega'!$B$6:$B$9,$A87,'Entrega'!$E$6:$E$9,"Víctor")+COUNTIFS('Entrega'!$B$6:$B$9,$A87,'Entrega'!$E$6:$E$9,"Ambos")+COUNTIFS('Defensa'!$B$6:$B$10,$A87,'Defensa'!$E$6:$E$10,"Víctor")+COUNTIFS('Defensa'!$B$6:$B$10,$A87,'Defensa'!$E$6:$E$10,"Ambos")</f>
         <v/>
       </c>
       <c r="G87" s="21">
-        <f>COUNTIFS('S1'!$B$6:$B$32,$A87,'S1'!$E$6:$E$32,"Diego")+COUNTIFS('S1'!$B$6:$B$32,$A87,'S1'!$E$6:$E$32,"Ambos")+COUNTIFS('S2'!$B$6:$B$23,$A87,'S2'!$E$6:$E$23,"Diego")+COUNTIFS('S2'!$B$6:$B$23,$A87,'S2'!$E$6:$E$23,"Ambos")+COUNTIFS('S3'!$B$6:$B$19,$A87,'S3'!$E$6:$E$19,"Diego")+COUNTIFS('S3'!$B$6:$B$19,$A87,'S3'!$E$6:$E$19,"Ambos")+COUNTIFS('S4'!$B$6:$B$20,$A87,'S4'!$E$6:$E$20,"Diego")+COUNTIFS('S4'!$B$6:$B$20,$A87,'S4'!$E$6:$E$20,"Ambos")+COUNTIFS('S5'!$B$6:$B$20,$A87,'S5'!$E$6:$E$20,"Diego")+COUNTIFS('S5'!$B$6:$B$20,$A87,'S5'!$E$6:$E$20,"Ambos")+COUNTIFS('S6'!$B$6:$B$17,$A87,'S6'!$E$6:$E$17,"Diego")+COUNTIFS('S6'!$B$6:$B$17,$A87,'S6'!$E$6:$E$17,"Ambos")+COUNTIFS('S7'!$B$6:$B$19,$A87,'S7'!$E$6:$E$19,"Diego")+COUNTIFS('S7'!$B$6:$B$19,$A87,'S7'!$E$6:$E$19,"Ambos")+COUNTIFS('S8'!$B$6:$B$23,$A87,'S8'!$E$6:$E$23,"Diego")+COUNTIFS('S8'!$B$6:$B$23,$A87,'S8'!$E$6:$E$23,"Ambos")+COUNTIFS('S9'!$B$6:$B$15,$A87,'S9'!$E$6:$E$15,"Diego")+COUNTIFS('S9'!$B$6:$B$15,$A87,'S9'!$E$6:$E$15,"Ambos")+COUNTIFS('S10'!$B$6:$B$13,$A87,'S10'!$E$6:$E$13,"Diego")+COUNTIFS('S10'!$B$6:$B$13,$A87,'S10'!$E$6:$E$13,"Ambos")+COUNTIFS('Holgura'!$B$6:$B$11,$A87,'Holgura'!$E$6:$E$11,"Diego")+COUNTIFS('Holgura'!$B$6:$B$11,$A87,'Holgura'!$E$6:$E$11,"Ambos")+COUNTIFS('Entrega'!$B$6:$B$9,$A87,'Entrega'!$E$6:$E$9,"Diego")+COUNTIFS('Entrega'!$B$6:$B$9,$A87,'Entrega'!$E$6:$E$9,"Ambos")+COUNTIFS('Defensa'!$B$6:$B$10,$A87,'Defensa'!$E$6:$E$10,"Diego")+COUNTIFS('Defensa'!$B$6:$B$10,$A87,'Defensa'!$E$6:$E$10,"Ambos")</f>
+        <f>COUNTIFS('S1'!$B$6:$B$32,$A87,'S1'!$E$6:$E$32,"Diego")+COUNTIFS('S1'!$B$6:$B$32,$A87,'S1'!$E$6:$E$32,"Ambos")+COUNTIFS('S2'!$B$6:$B$23,$A87,'S2'!$E$6:$E$23,"Diego")+COUNTIFS('S2'!$B$6:$B$23,$A87,'S2'!$E$6:$E$23,"Ambos")+COUNTIFS('S3'!$B$6:$B$24,$A87,'S3'!$E$6:$E$24,"Diego")+COUNTIFS('S3'!$B$6:$B$24,$A87,'S3'!$E$6:$E$24,"Ambos")+COUNTIFS('S4'!$B$6:$B$22,$A87,'S4'!$E$6:$E$22,"Diego")+COUNTIFS('S4'!$B$6:$B$22,$A87,'S4'!$E$6:$E$22,"Ambos")+COUNTIFS('S5'!$B$6:$B$20,$A87,'S5'!$E$6:$E$20,"Diego")+COUNTIFS('S5'!$B$6:$B$20,$A87,'S5'!$E$6:$E$20,"Ambos")+COUNTIFS('S6'!$B$6:$B$17,$A87,'S6'!$E$6:$E$17,"Diego")+COUNTIFS('S6'!$B$6:$B$17,$A87,'S6'!$E$6:$E$17,"Ambos")+COUNTIFS('S7'!$B$6:$B$19,$A87,'S7'!$E$6:$E$19,"Diego")+COUNTIFS('S7'!$B$6:$B$19,$A87,'S7'!$E$6:$E$19,"Ambos")+COUNTIFS('S8'!$B$6:$B$23,$A87,'S8'!$E$6:$E$23,"Diego")+COUNTIFS('S8'!$B$6:$B$23,$A87,'S8'!$E$6:$E$23,"Ambos")+COUNTIFS('S9'!$B$6:$B$15,$A87,'S9'!$E$6:$E$15,"Diego")+COUNTIFS('S9'!$B$6:$B$15,$A87,'S9'!$E$6:$E$15,"Ambos")+COUNTIFS('S10'!$B$6:$B$13,$A87,'S10'!$E$6:$E$13,"Diego")+COUNTIFS('S10'!$B$6:$B$13,$A87,'S10'!$E$6:$E$13,"Ambos")+COUNTIFS('Holgura'!$B$6:$B$11,$A87,'Holgura'!$E$6:$E$11,"Diego")+COUNTIFS('Holgura'!$B$6:$B$11,$A87,'Holgura'!$E$6:$E$11,"Ambos")+COUNTIFS('Entrega'!$B$6:$B$9,$A87,'Entrega'!$E$6:$E$9,"Diego")+COUNTIFS('Entrega'!$B$6:$B$9,$A87,'Entrega'!$E$6:$E$9,"Ambos")+COUNTIFS('Defensa'!$B$6:$B$10,$A87,'Defensa'!$E$6:$E$10,"Diego")+COUNTIFS('Defensa'!$B$6:$B$10,$A87,'Defensa'!$E$6:$E$10,"Ambos")</f>
         <v/>
       </c>
     </row>
@@ -11087,19 +11108,19 @@
         <v/>
       </c>
       <c r="D88" s="21">
-        <f>SUMIFS('S1'!$I$6:$I$32,'S1'!$B$6:$B$32,$A88,'S1'!$E$6:$E$32,"Víctor")+SUMIFS('S1'!$I$6:$I$32,'S1'!$B$6:$B$32,$A88,'S1'!$E$6:$E$32,"Ambos")+SUMIFS('S2'!$I$6:$I$23,'S2'!$B$6:$B$23,$A88,'S2'!$E$6:$E$23,"Víctor")+SUMIFS('S2'!$I$6:$I$23,'S2'!$B$6:$B$23,$A88,'S2'!$E$6:$E$23,"Ambos")+SUMIFS('S3'!$I$6:$I$19,'S3'!$B$6:$B$19,$A88,'S3'!$E$6:$E$19,"Víctor")+SUMIFS('S3'!$I$6:$I$19,'S3'!$B$6:$B$19,$A88,'S3'!$E$6:$E$19,"Ambos")+SUMIFS('S4'!$I$6:$I$20,'S4'!$B$6:$B$20,$A88,'S4'!$E$6:$E$20,"Víctor")+SUMIFS('S4'!$I$6:$I$20,'S4'!$B$6:$B$20,$A88,'S4'!$E$6:$E$20,"Ambos")+SUMIFS('S5'!$I$6:$I$20,'S5'!$B$6:$B$20,$A88,'S5'!$E$6:$E$20,"Víctor")+SUMIFS('S5'!$I$6:$I$20,'S5'!$B$6:$B$20,$A88,'S5'!$E$6:$E$20,"Ambos")+SUMIFS('S6'!$I$6:$I$17,'S6'!$B$6:$B$17,$A88,'S6'!$E$6:$E$17,"Víctor")+SUMIFS('S6'!$I$6:$I$17,'S6'!$B$6:$B$17,$A88,'S6'!$E$6:$E$17,"Ambos")+SUMIFS('S7'!$I$6:$I$19,'S7'!$B$6:$B$19,$A88,'S7'!$E$6:$E$19,"Víctor")+SUMIFS('S7'!$I$6:$I$19,'S7'!$B$6:$B$19,$A88,'S7'!$E$6:$E$19,"Ambos")+SUMIFS('S8'!$I$6:$I$23,'S8'!$B$6:$B$23,$A88,'S8'!$E$6:$E$23,"Víctor")+SUMIFS('S8'!$I$6:$I$23,'S8'!$B$6:$B$23,$A88,'S8'!$E$6:$E$23,"Ambos")+SUMIFS('S9'!$I$6:$I$15,'S9'!$B$6:$B$15,$A88,'S9'!$E$6:$E$15,"Víctor")+SUMIFS('S9'!$I$6:$I$15,'S9'!$B$6:$B$15,$A88,'S9'!$E$6:$E$15,"Ambos")+SUMIFS('S10'!$I$6:$I$13,'S10'!$B$6:$B$13,$A88,'S10'!$E$6:$E$13,"Víctor")+SUMIFS('S10'!$I$6:$I$13,'S10'!$B$6:$B$13,$A88,'S10'!$E$6:$E$13,"Ambos")+SUMIFS('Holgura'!$I$6:$I$11,'Holgura'!$B$6:$B$11,$A88,'Holgura'!$E$6:$E$11,"Víctor")+SUMIFS('Holgura'!$I$6:$I$11,'Holgura'!$B$6:$B$11,$A88,'Holgura'!$E$6:$E$11,"Ambos")+SUMIFS('Entrega'!$I$6:$I$9,'Entrega'!$B$6:$B$9,$A88,'Entrega'!$E$6:$E$9,"Víctor")+SUMIFS('Entrega'!$I$6:$I$9,'Entrega'!$B$6:$B$9,$A88,'Entrega'!$E$6:$E$9,"Ambos")+SUMIFS('Defensa'!$I$6:$I$10,'Defensa'!$B$6:$B$10,$A88,'Defensa'!$E$6:$E$10,"Víctor")+SUMIFS('Defensa'!$I$6:$I$10,'Defensa'!$B$6:$B$10,$A88,'Defensa'!$E$6:$E$10,"Ambos")</f>
+        <f>SUMIFS('S1'!$I$6:$I$32,'S1'!$B$6:$B$32,$A88,'S1'!$E$6:$E$32,"Víctor")+SUMIFS('S1'!$I$6:$I$32,'S1'!$B$6:$B$32,$A88,'S1'!$E$6:$E$32,"Ambos")+SUMIFS('S2'!$I$6:$I$23,'S2'!$B$6:$B$23,$A88,'S2'!$E$6:$E$23,"Víctor")+SUMIFS('S2'!$I$6:$I$23,'S2'!$B$6:$B$23,$A88,'S2'!$E$6:$E$23,"Ambos")+SUMIFS('S3'!$I$6:$I$24,'S3'!$B$6:$B$24,$A88,'S3'!$E$6:$E$24,"Víctor")+SUMIFS('S3'!$I$6:$I$24,'S3'!$B$6:$B$24,$A88,'S3'!$E$6:$E$24,"Ambos")+SUMIFS('S4'!$I$6:$I$22,'S4'!$B$6:$B$22,$A88,'S4'!$E$6:$E$22,"Víctor")+SUMIFS('S4'!$I$6:$I$22,'S4'!$B$6:$B$22,$A88,'S4'!$E$6:$E$22,"Ambos")+SUMIFS('S5'!$I$6:$I$20,'S5'!$B$6:$B$20,$A88,'S5'!$E$6:$E$20,"Víctor")+SUMIFS('S5'!$I$6:$I$20,'S5'!$B$6:$B$20,$A88,'S5'!$E$6:$E$20,"Ambos")+SUMIFS('S6'!$I$6:$I$17,'S6'!$B$6:$B$17,$A88,'S6'!$E$6:$E$17,"Víctor")+SUMIFS('S6'!$I$6:$I$17,'S6'!$B$6:$B$17,$A88,'S6'!$E$6:$E$17,"Ambos")+SUMIFS('S7'!$I$6:$I$19,'S7'!$B$6:$B$19,$A88,'S7'!$E$6:$E$19,"Víctor")+SUMIFS('S7'!$I$6:$I$19,'S7'!$B$6:$B$19,$A88,'S7'!$E$6:$E$19,"Ambos")+SUMIFS('S8'!$I$6:$I$23,'S8'!$B$6:$B$23,$A88,'S8'!$E$6:$E$23,"Víctor")+SUMIFS('S8'!$I$6:$I$23,'S8'!$B$6:$B$23,$A88,'S8'!$E$6:$E$23,"Ambos")+SUMIFS('S9'!$I$6:$I$15,'S9'!$B$6:$B$15,$A88,'S9'!$E$6:$E$15,"Víctor")+SUMIFS('S9'!$I$6:$I$15,'S9'!$B$6:$B$15,$A88,'S9'!$E$6:$E$15,"Ambos")+SUMIFS('S10'!$I$6:$I$13,'S10'!$B$6:$B$13,$A88,'S10'!$E$6:$E$13,"Víctor")+SUMIFS('S10'!$I$6:$I$13,'S10'!$B$6:$B$13,$A88,'S10'!$E$6:$E$13,"Ambos")+SUMIFS('Holgura'!$I$6:$I$11,'Holgura'!$B$6:$B$11,$A88,'Holgura'!$E$6:$E$11,"Víctor")+SUMIFS('Holgura'!$I$6:$I$11,'Holgura'!$B$6:$B$11,$A88,'Holgura'!$E$6:$E$11,"Ambos")+SUMIFS('Entrega'!$I$6:$I$9,'Entrega'!$B$6:$B$9,$A88,'Entrega'!$E$6:$E$9,"Víctor")+SUMIFS('Entrega'!$I$6:$I$9,'Entrega'!$B$6:$B$9,$A88,'Entrega'!$E$6:$E$9,"Ambos")+SUMIFS('Defensa'!$I$6:$I$10,'Defensa'!$B$6:$B$10,$A88,'Defensa'!$E$6:$E$10,"Víctor")+SUMIFS('Defensa'!$I$6:$I$10,'Defensa'!$B$6:$B$10,$A88,'Defensa'!$E$6:$E$10,"Ambos")</f>
         <v/>
       </c>
       <c r="E88" s="21">
-        <f>SUMIFS('S1'!$I$6:$I$32,'S1'!$B$6:$B$32,$A88,'S1'!$E$6:$E$32,"Diego")+SUMIFS('S1'!$I$6:$I$32,'S1'!$B$6:$B$32,$A88,'S1'!$E$6:$E$32,"Ambos")+SUMIFS('S2'!$I$6:$I$23,'S2'!$B$6:$B$23,$A88,'S2'!$E$6:$E$23,"Diego")+SUMIFS('S2'!$I$6:$I$23,'S2'!$B$6:$B$23,$A88,'S2'!$E$6:$E$23,"Ambos")+SUMIFS('S3'!$I$6:$I$19,'S3'!$B$6:$B$19,$A88,'S3'!$E$6:$E$19,"Diego")+SUMIFS('S3'!$I$6:$I$19,'S3'!$B$6:$B$19,$A88,'S3'!$E$6:$E$19,"Ambos")+SUMIFS('S4'!$I$6:$I$20,'S4'!$B$6:$B$20,$A88,'S4'!$E$6:$E$20,"Diego")+SUMIFS('S4'!$I$6:$I$20,'S4'!$B$6:$B$20,$A88,'S4'!$E$6:$E$20,"Ambos")+SUMIFS('S5'!$I$6:$I$20,'S5'!$B$6:$B$20,$A88,'S5'!$E$6:$E$20,"Diego")+SUMIFS('S5'!$I$6:$I$20,'S5'!$B$6:$B$20,$A88,'S5'!$E$6:$E$20,"Ambos")+SUMIFS('S6'!$I$6:$I$17,'S6'!$B$6:$B$17,$A88,'S6'!$E$6:$E$17,"Diego")+SUMIFS('S6'!$I$6:$I$17,'S6'!$B$6:$B$17,$A88,'S6'!$E$6:$E$17,"Ambos")+SUMIFS('S7'!$I$6:$I$19,'S7'!$B$6:$B$19,$A88,'S7'!$E$6:$E$19,"Diego")+SUMIFS('S7'!$I$6:$I$19,'S7'!$B$6:$B$19,$A88,'S7'!$E$6:$E$19,"Ambos")+SUMIFS('S8'!$I$6:$I$23,'S8'!$B$6:$B$23,$A88,'S8'!$E$6:$E$23,"Diego")+SUMIFS('S8'!$I$6:$I$23,'S8'!$B$6:$B$23,$A88,'S8'!$E$6:$E$23,"Ambos")+SUMIFS('S9'!$I$6:$I$15,'S9'!$B$6:$B$15,$A88,'S9'!$E$6:$E$15,"Diego")+SUMIFS('S9'!$I$6:$I$15,'S9'!$B$6:$B$15,$A88,'S9'!$E$6:$E$15,"Ambos")+SUMIFS('S10'!$I$6:$I$13,'S10'!$B$6:$B$13,$A88,'S10'!$E$6:$E$13,"Diego")+SUMIFS('S10'!$I$6:$I$13,'S10'!$B$6:$B$13,$A88,'S10'!$E$6:$E$13,"Ambos")+SUMIFS('Holgura'!$I$6:$I$11,'Holgura'!$B$6:$B$11,$A88,'Holgura'!$E$6:$E$11,"Diego")+SUMIFS('Holgura'!$I$6:$I$11,'Holgura'!$B$6:$B$11,$A88,'Holgura'!$E$6:$E$11,"Ambos")+SUMIFS('Entrega'!$I$6:$I$9,'Entrega'!$B$6:$B$9,$A88,'Entrega'!$E$6:$E$9,"Diego")+SUMIFS('Entrega'!$I$6:$I$9,'Entrega'!$B$6:$B$9,$A88,'Entrega'!$E$6:$E$9,"Ambos")+SUMIFS('Defensa'!$I$6:$I$10,'Defensa'!$B$6:$B$10,$A88,'Defensa'!$E$6:$E$10,"Diego")+SUMIFS('Defensa'!$I$6:$I$10,'Defensa'!$B$6:$B$10,$A88,'Defensa'!$E$6:$E$10,"Ambos")</f>
+        <f>SUMIFS('S1'!$I$6:$I$32,'S1'!$B$6:$B$32,$A88,'S1'!$E$6:$E$32,"Diego")+SUMIFS('S1'!$I$6:$I$32,'S1'!$B$6:$B$32,$A88,'S1'!$E$6:$E$32,"Ambos")+SUMIFS('S2'!$I$6:$I$23,'S2'!$B$6:$B$23,$A88,'S2'!$E$6:$E$23,"Diego")+SUMIFS('S2'!$I$6:$I$23,'S2'!$B$6:$B$23,$A88,'S2'!$E$6:$E$23,"Ambos")+SUMIFS('S3'!$I$6:$I$24,'S3'!$B$6:$B$24,$A88,'S3'!$E$6:$E$24,"Diego")+SUMIFS('S3'!$I$6:$I$24,'S3'!$B$6:$B$24,$A88,'S3'!$E$6:$E$24,"Ambos")+SUMIFS('S4'!$I$6:$I$22,'S4'!$B$6:$B$22,$A88,'S4'!$E$6:$E$22,"Diego")+SUMIFS('S4'!$I$6:$I$22,'S4'!$B$6:$B$22,$A88,'S4'!$E$6:$E$22,"Ambos")+SUMIFS('S5'!$I$6:$I$20,'S5'!$B$6:$B$20,$A88,'S5'!$E$6:$E$20,"Diego")+SUMIFS('S5'!$I$6:$I$20,'S5'!$B$6:$B$20,$A88,'S5'!$E$6:$E$20,"Ambos")+SUMIFS('S6'!$I$6:$I$17,'S6'!$B$6:$B$17,$A88,'S6'!$E$6:$E$17,"Diego")+SUMIFS('S6'!$I$6:$I$17,'S6'!$B$6:$B$17,$A88,'S6'!$E$6:$E$17,"Ambos")+SUMIFS('S7'!$I$6:$I$19,'S7'!$B$6:$B$19,$A88,'S7'!$E$6:$E$19,"Diego")+SUMIFS('S7'!$I$6:$I$19,'S7'!$B$6:$B$19,$A88,'S7'!$E$6:$E$19,"Ambos")+SUMIFS('S8'!$I$6:$I$23,'S8'!$B$6:$B$23,$A88,'S8'!$E$6:$E$23,"Diego")+SUMIFS('S8'!$I$6:$I$23,'S8'!$B$6:$B$23,$A88,'S8'!$E$6:$E$23,"Ambos")+SUMIFS('S9'!$I$6:$I$15,'S9'!$B$6:$B$15,$A88,'S9'!$E$6:$E$15,"Diego")+SUMIFS('S9'!$I$6:$I$15,'S9'!$B$6:$B$15,$A88,'S9'!$E$6:$E$15,"Ambos")+SUMIFS('S10'!$I$6:$I$13,'S10'!$B$6:$B$13,$A88,'S10'!$E$6:$E$13,"Diego")+SUMIFS('S10'!$I$6:$I$13,'S10'!$B$6:$B$13,$A88,'S10'!$E$6:$E$13,"Ambos")+SUMIFS('Holgura'!$I$6:$I$11,'Holgura'!$B$6:$B$11,$A88,'Holgura'!$E$6:$E$11,"Diego")+SUMIFS('Holgura'!$I$6:$I$11,'Holgura'!$B$6:$B$11,$A88,'Holgura'!$E$6:$E$11,"Ambos")+SUMIFS('Entrega'!$I$6:$I$9,'Entrega'!$B$6:$B$9,$A88,'Entrega'!$E$6:$E$9,"Diego")+SUMIFS('Entrega'!$I$6:$I$9,'Entrega'!$B$6:$B$9,$A88,'Entrega'!$E$6:$E$9,"Ambos")+SUMIFS('Defensa'!$I$6:$I$10,'Defensa'!$B$6:$B$10,$A88,'Defensa'!$E$6:$E$10,"Diego")+SUMIFS('Defensa'!$I$6:$I$10,'Defensa'!$B$6:$B$10,$A88,'Defensa'!$E$6:$E$10,"Ambos")</f>
         <v/>
       </c>
       <c r="F88" s="21">
-        <f>COUNTIFS('S1'!$B$6:$B$32,$A88,'S1'!$E$6:$E$32,"Víctor")+COUNTIFS('S1'!$B$6:$B$32,$A88,'S1'!$E$6:$E$32,"Ambos")+COUNTIFS('S2'!$B$6:$B$23,$A88,'S2'!$E$6:$E$23,"Víctor")+COUNTIFS('S2'!$B$6:$B$23,$A88,'S2'!$E$6:$E$23,"Ambos")+COUNTIFS('S3'!$B$6:$B$19,$A88,'S3'!$E$6:$E$19,"Víctor")+COUNTIFS('S3'!$B$6:$B$19,$A88,'S3'!$E$6:$E$19,"Ambos")+COUNTIFS('S4'!$B$6:$B$20,$A88,'S4'!$E$6:$E$20,"Víctor")+COUNTIFS('S4'!$B$6:$B$20,$A88,'S4'!$E$6:$E$20,"Ambos")+COUNTIFS('S5'!$B$6:$B$20,$A88,'S5'!$E$6:$E$20,"Víctor")+COUNTIFS('S5'!$B$6:$B$20,$A88,'S5'!$E$6:$E$20,"Ambos")+COUNTIFS('S6'!$B$6:$B$17,$A88,'S6'!$E$6:$E$17,"Víctor")+COUNTIFS('S6'!$B$6:$B$17,$A88,'S6'!$E$6:$E$17,"Ambos")+COUNTIFS('S7'!$B$6:$B$19,$A88,'S7'!$E$6:$E$19,"Víctor")+COUNTIFS('S7'!$B$6:$B$19,$A88,'S7'!$E$6:$E$19,"Ambos")+COUNTIFS('S8'!$B$6:$B$23,$A88,'S8'!$E$6:$E$23,"Víctor")+COUNTIFS('S8'!$B$6:$B$23,$A88,'S8'!$E$6:$E$23,"Ambos")+COUNTIFS('S9'!$B$6:$B$15,$A88,'S9'!$E$6:$E$15,"Víctor")+COUNTIFS('S9'!$B$6:$B$15,$A88,'S9'!$E$6:$E$15,"Ambos")+COUNTIFS('S10'!$B$6:$B$13,$A88,'S10'!$E$6:$E$13,"Víctor")+COUNTIFS('S10'!$B$6:$B$13,$A88,'S10'!$E$6:$E$13,"Ambos")+COUNTIFS('Holgura'!$B$6:$B$11,$A88,'Holgura'!$E$6:$E$11,"Víctor")+COUNTIFS('Holgura'!$B$6:$B$11,$A88,'Holgura'!$E$6:$E$11,"Ambos")+COUNTIFS('Entrega'!$B$6:$B$9,$A88,'Entrega'!$E$6:$E$9,"Víctor")+COUNTIFS('Entrega'!$B$6:$B$9,$A88,'Entrega'!$E$6:$E$9,"Ambos")+COUNTIFS('Defensa'!$B$6:$B$10,$A88,'Defensa'!$E$6:$E$10,"Víctor")+COUNTIFS('Defensa'!$B$6:$B$10,$A88,'Defensa'!$E$6:$E$10,"Ambos")</f>
+        <f>COUNTIFS('S1'!$B$6:$B$32,$A88,'S1'!$E$6:$E$32,"Víctor")+COUNTIFS('S1'!$B$6:$B$32,$A88,'S1'!$E$6:$E$32,"Ambos")+COUNTIFS('S2'!$B$6:$B$23,$A88,'S2'!$E$6:$E$23,"Víctor")+COUNTIFS('S2'!$B$6:$B$23,$A88,'S2'!$E$6:$E$23,"Ambos")+COUNTIFS('S3'!$B$6:$B$24,$A88,'S3'!$E$6:$E$24,"Víctor")+COUNTIFS('S3'!$B$6:$B$24,$A88,'S3'!$E$6:$E$24,"Ambos")+COUNTIFS('S4'!$B$6:$B$22,$A88,'S4'!$E$6:$E$22,"Víctor")+COUNTIFS('S4'!$B$6:$B$22,$A88,'S4'!$E$6:$E$22,"Ambos")+COUNTIFS('S5'!$B$6:$B$20,$A88,'S5'!$E$6:$E$20,"Víctor")+COUNTIFS('S5'!$B$6:$B$20,$A88,'S5'!$E$6:$E$20,"Ambos")+COUNTIFS('S6'!$B$6:$B$17,$A88,'S6'!$E$6:$E$17,"Víctor")+COUNTIFS('S6'!$B$6:$B$17,$A88,'S6'!$E$6:$E$17,"Ambos")+COUNTIFS('S7'!$B$6:$B$19,$A88,'S7'!$E$6:$E$19,"Víctor")+COUNTIFS('S7'!$B$6:$B$19,$A88,'S7'!$E$6:$E$19,"Ambos")+COUNTIFS('S8'!$B$6:$B$23,$A88,'S8'!$E$6:$E$23,"Víctor")+COUNTIFS('S8'!$B$6:$B$23,$A88,'S8'!$E$6:$E$23,"Ambos")+COUNTIFS('S9'!$B$6:$B$15,$A88,'S9'!$E$6:$E$15,"Víctor")+COUNTIFS('S9'!$B$6:$B$15,$A88,'S9'!$E$6:$E$15,"Ambos")+COUNTIFS('S10'!$B$6:$B$13,$A88,'S10'!$E$6:$E$13,"Víctor")+COUNTIFS('S10'!$B$6:$B$13,$A88,'S10'!$E$6:$E$13,"Ambos")+COUNTIFS('Holgura'!$B$6:$B$11,$A88,'Holgura'!$E$6:$E$11,"Víctor")+COUNTIFS('Holgura'!$B$6:$B$11,$A88,'Holgura'!$E$6:$E$11,"Ambos")+COUNTIFS('Entrega'!$B$6:$B$9,$A88,'Entrega'!$E$6:$E$9,"Víctor")+COUNTIFS('Entrega'!$B$6:$B$9,$A88,'Entrega'!$E$6:$E$9,"Ambos")+COUNTIFS('Defensa'!$B$6:$B$10,$A88,'Defensa'!$E$6:$E$10,"Víctor")+COUNTIFS('Defensa'!$B$6:$B$10,$A88,'Defensa'!$E$6:$E$10,"Ambos")</f>
         <v/>
       </c>
       <c r="G88" s="21">
-        <f>COUNTIFS('S1'!$B$6:$B$32,$A88,'S1'!$E$6:$E$32,"Diego")+COUNTIFS('S1'!$B$6:$B$32,$A88,'S1'!$E$6:$E$32,"Ambos")+COUNTIFS('S2'!$B$6:$B$23,$A88,'S2'!$E$6:$E$23,"Diego")+COUNTIFS('S2'!$B$6:$B$23,$A88,'S2'!$E$6:$E$23,"Ambos")+COUNTIFS('S3'!$B$6:$B$19,$A88,'S3'!$E$6:$E$19,"Diego")+COUNTIFS('S3'!$B$6:$B$19,$A88,'S3'!$E$6:$E$19,"Ambos")+COUNTIFS('S4'!$B$6:$B$20,$A88,'S4'!$E$6:$E$20,"Diego")+COUNTIFS('S4'!$B$6:$B$20,$A88,'S4'!$E$6:$E$20,"Ambos")+COUNTIFS('S5'!$B$6:$B$20,$A88,'S5'!$E$6:$E$20,"Diego")+COUNTIFS('S5'!$B$6:$B$20,$A88,'S5'!$E$6:$E$20,"Ambos")+COUNTIFS('S6'!$B$6:$B$17,$A88,'S6'!$E$6:$E$17,"Diego")+COUNTIFS('S6'!$B$6:$B$17,$A88,'S6'!$E$6:$E$17,"Ambos")+COUNTIFS('S7'!$B$6:$B$19,$A88,'S7'!$E$6:$E$19,"Diego")+COUNTIFS('S7'!$B$6:$B$19,$A88,'S7'!$E$6:$E$19,"Ambos")+COUNTIFS('S8'!$B$6:$B$23,$A88,'S8'!$E$6:$E$23,"Diego")+COUNTIFS('S8'!$B$6:$B$23,$A88,'S8'!$E$6:$E$23,"Ambos")+COUNTIFS('S9'!$B$6:$B$15,$A88,'S9'!$E$6:$E$15,"Diego")+COUNTIFS('S9'!$B$6:$B$15,$A88,'S9'!$E$6:$E$15,"Ambos")+COUNTIFS('S10'!$B$6:$B$13,$A88,'S10'!$E$6:$E$13,"Diego")+COUNTIFS('S10'!$B$6:$B$13,$A88,'S10'!$E$6:$E$13,"Ambos")+COUNTIFS('Holgura'!$B$6:$B$11,$A88,'Holgura'!$E$6:$E$11,"Diego")+COUNTIFS('Holgura'!$B$6:$B$11,$A88,'Holgura'!$E$6:$E$11,"Ambos")+COUNTIFS('Entrega'!$B$6:$B$9,$A88,'Entrega'!$E$6:$E$9,"Diego")+COUNTIFS('Entrega'!$B$6:$B$9,$A88,'Entrega'!$E$6:$E$9,"Ambos")+COUNTIFS('Defensa'!$B$6:$B$10,$A88,'Defensa'!$E$6:$E$10,"Diego")+COUNTIFS('Defensa'!$B$6:$B$10,$A88,'Defensa'!$E$6:$E$10,"Ambos")</f>
+        <f>COUNTIFS('S1'!$B$6:$B$32,$A88,'S1'!$E$6:$E$32,"Diego")+COUNTIFS('S1'!$B$6:$B$32,$A88,'S1'!$E$6:$E$32,"Ambos")+COUNTIFS('S2'!$B$6:$B$23,$A88,'S2'!$E$6:$E$23,"Diego")+COUNTIFS('S2'!$B$6:$B$23,$A88,'S2'!$E$6:$E$23,"Ambos")+COUNTIFS('S3'!$B$6:$B$24,$A88,'S3'!$E$6:$E$24,"Diego")+COUNTIFS('S3'!$B$6:$B$24,$A88,'S3'!$E$6:$E$24,"Ambos")+COUNTIFS('S4'!$B$6:$B$22,$A88,'S4'!$E$6:$E$22,"Diego")+COUNTIFS('S4'!$B$6:$B$22,$A88,'S4'!$E$6:$E$22,"Ambos")+COUNTIFS('S5'!$B$6:$B$20,$A88,'S5'!$E$6:$E$20,"Diego")+COUNTIFS('S5'!$B$6:$B$20,$A88,'S5'!$E$6:$E$20,"Ambos")+COUNTIFS('S6'!$B$6:$B$17,$A88,'S6'!$E$6:$E$17,"Diego")+COUNTIFS('S6'!$B$6:$B$17,$A88,'S6'!$E$6:$E$17,"Ambos")+COUNTIFS('S7'!$B$6:$B$19,$A88,'S7'!$E$6:$E$19,"Diego")+COUNTIFS('S7'!$B$6:$B$19,$A88,'S7'!$E$6:$E$19,"Ambos")+COUNTIFS('S8'!$B$6:$B$23,$A88,'S8'!$E$6:$E$23,"Diego")+COUNTIFS('S8'!$B$6:$B$23,$A88,'S8'!$E$6:$E$23,"Ambos")+COUNTIFS('S9'!$B$6:$B$15,$A88,'S9'!$E$6:$E$15,"Diego")+COUNTIFS('S9'!$B$6:$B$15,$A88,'S9'!$E$6:$E$15,"Ambos")+COUNTIFS('S10'!$B$6:$B$13,$A88,'S10'!$E$6:$E$13,"Diego")+COUNTIFS('S10'!$B$6:$B$13,$A88,'S10'!$E$6:$E$13,"Ambos")+COUNTIFS('Holgura'!$B$6:$B$11,$A88,'Holgura'!$E$6:$E$11,"Diego")+COUNTIFS('Holgura'!$B$6:$B$11,$A88,'Holgura'!$E$6:$E$11,"Ambos")+COUNTIFS('Entrega'!$B$6:$B$9,$A88,'Entrega'!$E$6:$E$9,"Diego")+COUNTIFS('Entrega'!$B$6:$B$9,$A88,'Entrega'!$E$6:$E$9,"Ambos")+COUNTIFS('Defensa'!$B$6:$B$10,$A88,'Defensa'!$E$6:$E$10,"Diego")+COUNTIFS('Defensa'!$B$6:$B$10,$A88,'Defensa'!$E$6:$E$10,"Ambos")</f>
         <v/>
       </c>
     </row>
@@ -11116,19 +11137,19 @@
         <v/>
       </c>
       <c r="D89" s="21">
-        <f>SUMIFS('S1'!$I$6:$I$32,'S1'!$B$6:$B$32,$A89,'S1'!$E$6:$E$32,"Víctor")+SUMIFS('S1'!$I$6:$I$32,'S1'!$B$6:$B$32,$A89,'S1'!$E$6:$E$32,"Ambos")+SUMIFS('S2'!$I$6:$I$23,'S2'!$B$6:$B$23,$A89,'S2'!$E$6:$E$23,"Víctor")+SUMIFS('S2'!$I$6:$I$23,'S2'!$B$6:$B$23,$A89,'S2'!$E$6:$E$23,"Ambos")+SUMIFS('S3'!$I$6:$I$19,'S3'!$B$6:$B$19,$A89,'S3'!$E$6:$E$19,"Víctor")+SUMIFS('S3'!$I$6:$I$19,'S3'!$B$6:$B$19,$A89,'S3'!$E$6:$E$19,"Ambos")+SUMIFS('S4'!$I$6:$I$20,'S4'!$B$6:$B$20,$A89,'S4'!$E$6:$E$20,"Víctor")+SUMIFS('S4'!$I$6:$I$20,'S4'!$B$6:$B$20,$A89,'S4'!$E$6:$E$20,"Ambos")+SUMIFS('S5'!$I$6:$I$20,'S5'!$B$6:$B$20,$A89,'S5'!$E$6:$E$20,"Víctor")+SUMIFS('S5'!$I$6:$I$20,'S5'!$B$6:$B$20,$A89,'S5'!$E$6:$E$20,"Ambos")+SUMIFS('S6'!$I$6:$I$17,'S6'!$B$6:$B$17,$A89,'S6'!$E$6:$E$17,"Víctor")+SUMIFS('S6'!$I$6:$I$17,'S6'!$B$6:$B$17,$A89,'S6'!$E$6:$E$17,"Ambos")+SUMIFS('S7'!$I$6:$I$19,'S7'!$B$6:$B$19,$A89,'S7'!$E$6:$E$19,"Víctor")+SUMIFS('S7'!$I$6:$I$19,'S7'!$B$6:$B$19,$A89,'S7'!$E$6:$E$19,"Ambos")+SUMIFS('S8'!$I$6:$I$23,'S8'!$B$6:$B$23,$A89,'S8'!$E$6:$E$23,"Víctor")+SUMIFS('S8'!$I$6:$I$23,'S8'!$B$6:$B$23,$A89,'S8'!$E$6:$E$23,"Ambos")+SUMIFS('S9'!$I$6:$I$15,'S9'!$B$6:$B$15,$A89,'S9'!$E$6:$E$15,"Víctor")+SUMIFS('S9'!$I$6:$I$15,'S9'!$B$6:$B$15,$A89,'S9'!$E$6:$E$15,"Ambos")+SUMIFS('S10'!$I$6:$I$13,'S10'!$B$6:$B$13,$A89,'S10'!$E$6:$E$13,"Víctor")+SUMIFS('S10'!$I$6:$I$13,'S10'!$B$6:$B$13,$A89,'S10'!$E$6:$E$13,"Ambos")+SUMIFS('Holgura'!$I$6:$I$11,'Holgura'!$B$6:$B$11,$A89,'Holgura'!$E$6:$E$11,"Víctor")+SUMIFS('Holgura'!$I$6:$I$11,'Holgura'!$B$6:$B$11,$A89,'Holgura'!$E$6:$E$11,"Ambos")+SUMIFS('Entrega'!$I$6:$I$9,'Entrega'!$B$6:$B$9,$A89,'Entrega'!$E$6:$E$9,"Víctor")+SUMIFS('Entrega'!$I$6:$I$9,'Entrega'!$B$6:$B$9,$A89,'Entrega'!$E$6:$E$9,"Ambos")+SUMIFS('Defensa'!$I$6:$I$10,'Defensa'!$B$6:$B$10,$A89,'Defensa'!$E$6:$E$10,"Víctor")+SUMIFS('Defensa'!$I$6:$I$10,'Defensa'!$B$6:$B$10,$A89,'Defensa'!$E$6:$E$10,"Ambos")</f>
+        <f>SUMIFS('S1'!$I$6:$I$32,'S1'!$B$6:$B$32,$A89,'S1'!$E$6:$E$32,"Víctor")+SUMIFS('S1'!$I$6:$I$32,'S1'!$B$6:$B$32,$A89,'S1'!$E$6:$E$32,"Ambos")+SUMIFS('S2'!$I$6:$I$23,'S2'!$B$6:$B$23,$A89,'S2'!$E$6:$E$23,"Víctor")+SUMIFS('S2'!$I$6:$I$23,'S2'!$B$6:$B$23,$A89,'S2'!$E$6:$E$23,"Ambos")+SUMIFS('S3'!$I$6:$I$24,'S3'!$B$6:$B$24,$A89,'S3'!$E$6:$E$24,"Víctor")+SUMIFS('S3'!$I$6:$I$24,'S3'!$B$6:$B$24,$A89,'S3'!$E$6:$E$24,"Ambos")+SUMIFS('S4'!$I$6:$I$22,'S4'!$B$6:$B$22,$A89,'S4'!$E$6:$E$22,"Víctor")+SUMIFS('S4'!$I$6:$I$22,'S4'!$B$6:$B$22,$A89,'S4'!$E$6:$E$22,"Ambos")+SUMIFS('S5'!$I$6:$I$20,'S5'!$B$6:$B$20,$A89,'S5'!$E$6:$E$20,"Víctor")+SUMIFS('S5'!$I$6:$I$20,'S5'!$B$6:$B$20,$A89,'S5'!$E$6:$E$20,"Ambos")+SUMIFS('S6'!$I$6:$I$17,'S6'!$B$6:$B$17,$A89,'S6'!$E$6:$E$17,"Víctor")+SUMIFS('S6'!$I$6:$I$17,'S6'!$B$6:$B$17,$A89,'S6'!$E$6:$E$17,"Ambos")+SUMIFS('S7'!$I$6:$I$19,'S7'!$B$6:$B$19,$A89,'S7'!$E$6:$E$19,"Víctor")+SUMIFS('S7'!$I$6:$I$19,'S7'!$B$6:$B$19,$A89,'S7'!$E$6:$E$19,"Ambos")+SUMIFS('S8'!$I$6:$I$23,'S8'!$B$6:$B$23,$A89,'S8'!$E$6:$E$23,"Víctor")+SUMIFS('S8'!$I$6:$I$23,'S8'!$B$6:$B$23,$A89,'S8'!$E$6:$E$23,"Ambos")+SUMIFS('S9'!$I$6:$I$15,'S9'!$B$6:$B$15,$A89,'S9'!$E$6:$E$15,"Víctor")+SUMIFS('S9'!$I$6:$I$15,'S9'!$B$6:$B$15,$A89,'S9'!$E$6:$E$15,"Ambos")+SUMIFS('S10'!$I$6:$I$13,'S10'!$B$6:$B$13,$A89,'S10'!$E$6:$E$13,"Víctor")+SUMIFS('S10'!$I$6:$I$13,'S10'!$B$6:$B$13,$A89,'S10'!$E$6:$E$13,"Ambos")+SUMIFS('Holgura'!$I$6:$I$11,'Holgura'!$B$6:$B$11,$A89,'Holgura'!$E$6:$E$11,"Víctor")+SUMIFS('Holgura'!$I$6:$I$11,'Holgura'!$B$6:$B$11,$A89,'Holgura'!$E$6:$E$11,"Ambos")+SUMIFS('Entrega'!$I$6:$I$9,'Entrega'!$B$6:$B$9,$A89,'Entrega'!$E$6:$E$9,"Víctor")+SUMIFS('Entrega'!$I$6:$I$9,'Entrega'!$B$6:$B$9,$A89,'Entrega'!$E$6:$E$9,"Ambos")+SUMIFS('Defensa'!$I$6:$I$10,'Defensa'!$B$6:$B$10,$A89,'Defensa'!$E$6:$E$10,"Víctor")+SUMIFS('Defensa'!$I$6:$I$10,'Defensa'!$B$6:$B$10,$A89,'Defensa'!$E$6:$E$10,"Ambos")</f>
         <v/>
       </c>
       <c r="E89" s="21">
-        <f>SUMIFS('S1'!$I$6:$I$32,'S1'!$B$6:$B$32,$A89,'S1'!$E$6:$E$32,"Diego")+SUMIFS('S1'!$I$6:$I$32,'S1'!$B$6:$B$32,$A89,'S1'!$E$6:$E$32,"Ambos")+SUMIFS('S2'!$I$6:$I$23,'S2'!$B$6:$B$23,$A89,'S2'!$E$6:$E$23,"Diego")+SUMIFS('S2'!$I$6:$I$23,'S2'!$B$6:$B$23,$A89,'S2'!$E$6:$E$23,"Ambos")+SUMIFS('S3'!$I$6:$I$19,'S3'!$B$6:$B$19,$A89,'S3'!$E$6:$E$19,"Diego")+SUMIFS('S3'!$I$6:$I$19,'S3'!$B$6:$B$19,$A89,'S3'!$E$6:$E$19,"Ambos")+SUMIFS('S4'!$I$6:$I$20,'S4'!$B$6:$B$20,$A89,'S4'!$E$6:$E$20,"Diego")+SUMIFS('S4'!$I$6:$I$20,'S4'!$B$6:$B$20,$A89,'S4'!$E$6:$E$20,"Ambos")+SUMIFS('S5'!$I$6:$I$20,'S5'!$B$6:$B$20,$A89,'S5'!$E$6:$E$20,"Diego")+SUMIFS('S5'!$I$6:$I$20,'S5'!$B$6:$B$20,$A89,'S5'!$E$6:$E$20,"Ambos")+SUMIFS('S6'!$I$6:$I$17,'S6'!$B$6:$B$17,$A89,'S6'!$E$6:$E$17,"Diego")+SUMIFS('S6'!$I$6:$I$17,'S6'!$B$6:$B$17,$A89,'S6'!$E$6:$E$17,"Ambos")+SUMIFS('S7'!$I$6:$I$19,'S7'!$B$6:$B$19,$A89,'S7'!$E$6:$E$19,"Diego")+SUMIFS('S7'!$I$6:$I$19,'S7'!$B$6:$B$19,$A89,'S7'!$E$6:$E$19,"Ambos")+SUMIFS('S8'!$I$6:$I$23,'S8'!$B$6:$B$23,$A89,'S8'!$E$6:$E$23,"Diego")+SUMIFS('S8'!$I$6:$I$23,'S8'!$B$6:$B$23,$A89,'S8'!$E$6:$E$23,"Ambos")+SUMIFS('S9'!$I$6:$I$15,'S9'!$B$6:$B$15,$A89,'S9'!$E$6:$E$15,"Diego")+SUMIFS('S9'!$I$6:$I$15,'S9'!$B$6:$B$15,$A89,'S9'!$E$6:$E$15,"Ambos")+SUMIFS('S10'!$I$6:$I$13,'S10'!$B$6:$B$13,$A89,'S10'!$E$6:$E$13,"Diego")+SUMIFS('S10'!$I$6:$I$13,'S10'!$B$6:$B$13,$A89,'S10'!$E$6:$E$13,"Ambos")+SUMIFS('Holgura'!$I$6:$I$11,'Holgura'!$B$6:$B$11,$A89,'Holgura'!$E$6:$E$11,"Diego")+SUMIFS('Holgura'!$I$6:$I$11,'Holgura'!$B$6:$B$11,$A89,'Holgura'!$E$6:$E$11,"Ambos")+SUMIFS('Entrega'!$I$6:$I$9,'Entrega'!$B$6:$B$9,$A89,'Entrega'!$E$6:$E$9,"Diego")+SUMIFS('Entrega'!$I$6:$I$9,'Entrega'!$B$6:$B$9,$A89,'Entrega'!$E$6:$E$9,"Ambos")+SUMIFS('Defensa'!$I$6:$I$10,'Defensa'!$B$6:$B$10,$A89,'Defensa'!$E$6:$E$10,"Diego")+SUMIFS('Defensa'!$I$6:$I$10,'Defensa'!$B$6:$B$10,$A89,'Defensa'!$E$6:$E$10,"Ambos")</f>
+        <f>SUMIFS('S1'!$I$6:$I$32,'S1'!$B$6:$B$32,$A89,'S1'!$E$6:$E$32,"Diego")+SUMIFS('S1'!$I$6:$I$32,'S1'!$B$6:$B$32,$A89,'S1'!$E$6:$E$32,"Ambos")+SUMIFS('S2'!$I$6:$I$23,'S2'!$B$6:$B$23,$A89,'S2'!$E$6:$E$23,"Diego")+SUMIFS('S2'!$I$6:$I$23,'S2'!$B$6:$B$23,$A89,'S2'!$E$6:$E$23,"Ambos")+SUMIFS('S3'!$I$6:$I$24,'S3'!$B$6:$B$24,$A89,'S3'!$E$6:$E$24,"Diego")+SUMIFS('S3'!$I$6:$I$24,'S3'!$B$6:$B$24,$A89,'S3'!$E$6:$E$24,"Ambos")+SUMIFS('S4'!$I$6:$I$22,'S4'!$B$6:$B$22,$A89,'S4'!$E$6:$E$22,"Diego")+SUMIFS('S4'!$I$6:$I$22,'S4'!$B$6:$B$22,$A89,'S4'!$E$6:$E$22,"Ambos")+SUMIFS('S5'!$I$6:$I$20,'S5'!$B$6:$B$20,$A89,'S5'!$E$6:$E$20,"Diego")+SUMIFS('S5'!$I$6:$I$20,'S5'!$B$6:$B$20,$A89,'S5'!$E$6:$E$20,"Ambos")+SUMIFS('S6'!$I$6:$I$17,'S6'!$B$6:$B$17,$A89,'S6'!$E$6:$E$17,"Diego")+SUMIFS('S6'!$I$6:$I$17,'S6'!$B$6:$B$17,$A89,'S6'!$E$6:$E$17,"Ambos")+SUMIFS('S7'!$I$6:$I$19,'S7'!$B$6:$B$19,$A89,'S7'!$E$6:$E$19,"Diego")+SUMIFS('S7'!$I$6:$I$19,'S7'!$B$6:$B$19,$A89,'S7'!$E$6:$E$19,"Ambos")+SUMIFS('S8'!$I$6:$I$23,'S8'!$B$6:$B$23,$A89,'S8'!$E$6:$E$23,"Diego")+SUMIFS('S8'!$I$6:$I$23,'S8'!$B$6:$B$23,$A89,'S8'!$E$6:$E$23,"Ambos")+SUMIFS('S9'!$I$6:$I$15,'S9'!$B$6:$B$15,$A89,'S9'!$E$6:$E$15,"Diego")+SUMIFS('S9'!$I$6:$I$15,'S9'!$B$6:$B$15,$A89,'S9'!$E$6:$E$15,"Ambos")+SUMIFS('S10'!$I$6:$I$13,'S10'!$B$6:$B$13,$A89,'S10'!$E$6:$E$13,"Diego")+SUMIFS('S10'!$I$6:$I$13,'S10'!$B$6:$B$13,$A89,'S10'!$E$6:$E$13,"Ambos")+SUMIFS('Holgura'!$I$6:$I$11,'Holgura'!$B$6:$B$11,$A89,'Holgura'!$E$6:$E$11,"Diego")+SUMIFS('Holgura'!$I$6:$I$11,'Holgura'!$B$6:$B$11,$A89,'Holgura'!$E$6:$E$11,"Ambos")+SUMIFS('Entrega'!$I$6:$I$9,'Entrega'!$B$6:$B$9,$A89,'Entrega'!$E$6:$E$9,"Diego")+SUMIFS('Entrega'!$I$6:$I$9,'Entrega'!$B$6:$B$9,$A89,'Entrega'!$E$6:$E$9,"Ambos")+SUMIFS('Defensa'!$I$6:$I$10,'Defensa'!$B$6:$B$10,$A89,'Defensa'!$E$6:$E$10,"Diego")+SUMIFS('Defensa'!$I$6:$I$10,'Defensa'!$B$6:$B$10,$A89,'Defensa'!$E$6:$E$10,"Ambos")</f>
         <v/>
       </c>
       <c r="F89" s="21">
-        <f>COUNTIFS('S1'!$B$6:$B$32,$A89,'S1'!$E$6:$E$32,"Víctor")+COUNTIFS('S1'!$B$6:$B$32,$A89,'S1'!$E$6:$E$32,"Ambos")+COUNTIFS('S2'!$B$6:$B$23,$A89,'S2'!$E$6:$E$23,"Víctor")+COUNTIFS('S2'!$B$6:$B$23,$A89,'S2'!$E$6:$E$23,"Ambos")+COUNTIFS('S3'!$B$6:$B$19,$A89,'S3'!$E$6:$E$19,"Víctor")+COUNTIFS('S3'!$B$6:$B$19,$A89,'S3'!$E$6:$E$19,"Ambos")+COUNTIFS('S4'!$B$6:$B$20,$A89,'S4'!$E$6:$E$20,"Víctor")+COUNTIFS('S4'!$B$6:$B$20,$A89,'S4'!$E$6:$E$20,"Ambos")+COUNTIFS('S5'!$B$6:$B$20,$A89,'S5'!$E$6:$E$20,"Víctor")+COUNTIFS('S5'!$B$6:$B$20,$A89,'S5'!$E$6:$E$20,"Ambos")+COUNTIFS('S6'!$B$6:$B$17,$A89,'S6'!$E$6:$E$17,"Víctor")+COUNTIFS('S6'!$B$6:$B$17,$A89,'S6'!$E$6:$E$17,"Ambos")+COUNTIFS('S7'!$B$6:$B$19,$A89,'S7'!$E$6:$E$19,"Víctor")+COUNTIFS('S7'!$B$6:$B$19,$A89,'S7'!$E$6:$E$19,"Ambos")+COUNTIFS('S8'!$B$6:$B$23,$A89,'S8'!$E$6:$E$23,"Víctor")+COUNTIFS('S8'!$B$6:$B$23,$A89,'S8'!$E$6:$E$23,"Ambos")+COUNTIFS('S9'!$B$6:$B$15,$A89,'S9'!$E$6:$E$15,"Víctor")+COUNTIFS('S9'!$B$6:$B$15,$A89,'S9'!$E$6:$E$15,"Ambos")+COUNTIFS('S10'!$B$6:$B$13,$A89,'S10'!$E$6:$E$13,"Víctor")+COUNTIFS('S10'!$B$6:$B$13,$A89,'S10'!$E$6:$E$13,"Ambos")+COUNTIFS('Holgura'!$B$6:$B$11,$A89,'Holgura'!$E$6:$E$11,"Víctor")+COUNTIFS('Holgura'!$B$6:$B$11,$A89,'Holgura'!$E$6:$E$11,"Ambos")+COUNTIFS('Entrega'!$B$6:$B$9,$A89,'Entrega'!$E$6:$E$9,"Víctor")+COUNTIFS('Entrega'!$B$6:$B$9,$A89,'Entrega'!$E$6:$E$9,"Ambos")+COUNTIFS('Defensa'!$B$6:$B$10,$A89,'Defensa'!$E$6:$E$10,"Víctor")+COUNTIFS('Defensa'!$B$6:$B$10,$A89,'Defensa'!$E$6:$E$10,"Ambos")</f>
+        <f>COUNTIFS('S1'!$B$6:$B$32,$A89,'S1'!$E$6:$E$32,"Víctor")+COUNTIFS('S1'!$B$6:$B$32,$A89,'S1'!$E$6:$E$32,"Ambos")+COUNTIFS('S2'!$B$6:$B$23,$A89,'S2'!$E$6:$E$23,"Víctor")+COUNTIFS('S2'!$B$6:$B$23,$A89,'S2'!$E$6:$E$23,"Ambos")+COUNTIFS('S3'!$B$6:$B$24,$A89,'S3'!$E$6:$E$24,"Víctor")+COUNTIFS('S3'!$B$6:$B$24,$A89,'S3'!$E$6:$E$24,"Ambos")+COUNTIFS('S4'!$B$6:$B$22,$A89,'S4'!$E$6:$E$22,"Víctor")+COUNTIFS('S4'!$B$6:$B$22,$A89,'S4'!$E$6:$E$22,"Ambos")+COUNTIFS('S5'!$B$6:$B$20,$A89,'S5'!$E$6:$E$20,"Víctor")+COUNTIFS('S5'!$B$6:$B$20,$A89,'S5'!$E$6:$E$20,"Ambos")+COUNTIFS('S6'!$B$6:$B$17,$A89,'S6'!$E$6:$E$17,"Víctor")+COUNTIFS('S6'!$B$6:$B$17,$A89,'S6'!$E$6:$E$17,"Ambos")+COUNTIFS('S7'!$B$6:$B$19,$A89,'S7'!$E$6:$E$19,"Víctor")+COUNTIFS('S7'!$B$6:$B$19,$A89,'S7'!$E$6:$E$19,"Ambos")+COUNTIFS('S8'!$B$6:$B$23,$A89,'S8'!$E$6:$E$23,"Víctor")+COUNTIFS('S8'!$B$6:$B$23,$A89,'S8'!$E$6:$E$23,"Ambos")+COUNTIFS('S9'!$B$6:$B$15,$A89,'S9'!$E$6:$E$15,"Víctor")+COUNTIFS('S9'!$B$6:$B$15,$A89,'S9'!$E$6:$E$15,"Ambos")+COUNTIFS('S10'!$B$6:$B$13,$A89,'S10'!$E$6:$E$13,"Víctor")+COUNTIFS('S10'!$B$6:$B$13,$A89,'S10'!$E$6:$E$13,"Ambos")+COUNTIFS('Holgura'!$B$6:$B$11,$A89,'Holgura'!$E$6:$E$11,"Víctor")+COUNTIFS('Holgura'!$B$6:$B$11,$A89,'Holgura'!$E$6:$E$11,"Ambos")+COUNTIFS('Entrega'!$B$6:$B$9,$A89,'Entrega'!$E$6:$E$9,"Víctor")+COUNTIFS('Entrega'!$B$6:$B$9,$A89,'Entrega'!$E$6:$E$9,"Ambos")+COUNTIFS('Defensa'!$B$6:$B$10,$A89,'Defensa'!$E$6:$E$10,"Víctor")+COUNTIFS('Defensa'!$B$6:$B$10,$A89,'Defensa'!$E$6:$E$10,"Ambos")</f>
         <v/>
       </c>
       <c r="G89" s="21">
-        <f>COUNTIFS('S1'!$B$6:$B$32,$A89,'S1'!$E$6:$E$32,"Diego")+COUNTIFS('S1'!$B$6:$B$32,$A89,'S1'!$E$6:$E$32,"Ambos")+COUNTIFS('S2'!$B$6:$B$23,$A89,'S2'!$E$6:$E$23,"Diego")+COUNTIFS('S2'!$B$6:$B$23,$A89,'S2'!$E$6:$E$23,"Ambos")+COUNTIFS('S3'!$B$6:$B$19,$A89,'S3'!$E$6:$E$19,"Diego")+COUNTIFS('S3'!$B$6:$B$19,$A89,'S3'!$E$6:$E$19,"Ambos")+COUNTIFS('S4'!$B$6:$B$20,$A89,'S4'!$E$6:$E$20,"Diego")+COUNTIFS('S4'!$B$6:$B$20,$A89,'S4'!$E$6:$E$20,"Ambos")+COUNTIFS('S5'!$B$6:$B$20,$A89,'S5'!$E$6:$E$20,"Diego")+COUNTIFS('S5'!$B$6:$B$20,$A89,'S5'!$E$6:$E$20,"Ambos")+COUNTIFS('S6'!$B$6:$B$17,$A89,'S6'!$E$6:$E$17,"Diego")+COUNTIFS('S6'!$B$6:$B$17,$A89,'S6'!$E$6:$E$17,"Ambos")+COUNTIFS('S7'!$B$6:$B$19,$A89,'S7'!$E$6:$E$19,"Diego")+COUNTIFS('S7'!$B$6:$B$19,$A89,'S7'!$E$6:$E$19,"Ambos")+COUNTIFS('S8'!$B$6:$B$23,$A89,'S8'!$E$6:$E$23,"Diego")+COUNTIFS('S8'!$B$6:$B$23,$A89,'S8'!$E$6:$E$23,"Ambos")+COUNTIFS('S9'!$B$6:$B$15,$A89,'S9'!$E$6:$E$15,"Diego")+COUNTIFS('S9'!$B$6:$B$15,$A89,'S9'!$E$6:$E$15,"Ambos")+COUNTIFS('S10'!$B$6:$B$13,$A89,'S10'!$E$6:$E$13,"Diego")+COUNTIFS('S10'!$B$6:$B$13,$A89,'S10'!$E$6:$E$13,"Ambos")+COUNTIFS('Holgura'!$B$6:$B$11,$A89,'Holgura'!$E$6:$E$11,"Diego")+COUNTIFS('Holgura'!$B$6:$B$11,$A89,'Holgura'!$E$6:$E$11,"Ambos")+COUNTIFS('Entrega'!$B$6:$B$9,$A89,'Entrega'!$E$6:$E$9,"Diego")+COUNTIFS('Entrega'!$B$6:$B$9,$A89,'Entrega'!$E$6:$E$9,"Ambos")+COUNTIFS('Defensa'!$B$6:$B$10,$A89,'Defensa'!$E$6:$E$10,"Diego")+COUNTIFS('Defensa'!$B$6:$B$10,$A89,'Defensa'!$E$6:$E$10,"Ambos")</f>
+        <f>COUNTIFS('S1'!$B$6:$B$32,$A89,'S1'!$E$6:$E$32,"Diego")+COUNTIFS('S1'!$B$6:$B$32,$A89,'S1'!$E$6:$E$32,"Ambos")+COUNTIFS('S2'!$B$6:$B$23,$A89,'S2'!$E$6:$E$23,"Diego")+COUNTIFS('S2'!$B$6:$B$23,$A89,'S2'!$E$6:$E$23,"Ambos")+COUNTIFS('S3'!$B$6:$B$24,$A89,'S3'!$E$6:$E$24,"Diego")+COUNTIFS('S3'!$B$6:$B$24,$A89,'S3'!$E$6:$E$24,"Ambos")+COUNTIFS('S4'!$B$6:$B$22,$A89,'S4'!$E$6:$E$22,"Diego")+COUNTIFS('S4'!$B$6:$B$22,$A89,'S4'!$E$6:$E$22,"Ambos")+COUNTIFS('S5'!$B$6:$B$20,$A89,'S5'!$E$6:$E$20,"Diego")+COUNTIFS('S5'!$B$6:$B$20,$A89,'S5'!$E$6:$E$20,"Ambos")+COUNTIFS('S6'!$B$6:$B$17,$A89,'S6'!$E$6:$E$17,"Diego")+COUNTIFS('S6'!$B$6:$B$17,$A89,'S6'!$E$6:$E$17,"Ambos")+COUNTIFS('S7'!$B$6:$B$19,$A89,'S7'!$E$6:$E$19,"Diego")+COUNTIFS('S7'!$B$6:$B$19,$A89,'S7'!$E$6:$E$19,"Ambos")+COUNTIFS('S8'!$B$6:$B$23,$A89,'S8'!$E$6:$E$23,"Diego")+COUNTIFS('S8'!$B$6:$B$23,$A89,'S8'!$E$6:$E$23,"Ambos")+COUNTIFS('S9'!$B$6:$B$15,$A89,'S9'!$E$6:$E$15,"Diego")+COUNTIFS('S9'!$B$6:$B$15,$A89,'S9'!$E$6:$E$15,"Ambos")+COUNTIFS('S10'!$B$6:$B$13,$A89,'S10'!$E$6:$E$13,"Diego")+COUNTIFS('S10'!$B$6:$B$13,$A89,'S10'!$E$6:$E$13,"Ambos")+COUNTIFS('Holgura'!$B$6:$B$11,$A89,'Holgura'!$E$6:$E$11,"Diego")+COUNTIFS('Holgura'!$B$6:$B$11,$A89,'Holgura'!$E$6:$E$11,"Ambos")+COUNTIFS('Entrega'!$B$6:$B$9,$A89,'Entrega'!$E$6:$E$9,"Diego")+COUNTIFS('Entrega'!$B$6:$B$9,$A89,'Entrega'!$E$6:$E$9,"Ambos")+COUNTIFS('Defensa'!$B$6:$B$10,$A89,'Defensa'!$E$6:$E$10,"Diego")+COUNTIFS('Defensa'!$B$6:$B$10,$A89,'Defensa'!$E$6:$E$10,"Ambos")</f>
         <v/>
       </c>
     </row>
@@ -11145,19 +11166,19 @@
         <v/>
       </c>
       <c r="D90" s="21">
-        <f>SUMIFS('S1'!$I$6:$I$32,'S1'!$B$6:$B$32,$A90,'S1'!$E$6:$E$32,"Víctor")+SUMIFS('S1'!$I$6:$I$32,'S1'!$B$6:$B$32,$A90,'S1'!$E$6:$E$32,"Ambos")+SUMIFS('S2'!$I$6:$I$23,'S2'!$B$6:$B$23,$A90,'S2'!$E$6:$E$23,"Víctor")+SUMIFS('S2'!$I$6:$I$23,'S2'!$B$6:$B$23,$A90,'S2'!$E$6:$E$23,"Ambos")+SUMIFS('S3'!$I$6:$I$19,'S3'!$B$6:$B$19,$A90,'S3'!$E$6:$E$19,"Víctor")+SUMIFS('S3'!$I$6:$I$19,'S3'!$B$6:$B$19,$A90,'S3'!$E$6:$E$19,"Ambos")+SUMIFS('S4'!$I$6:$I$20,'S4'!$B$6:$B$20,$A90,'S4'!$E$6:$E$20,"Víctor")+SUMIFS('S4'!$I$6:$I$20,'S4'!$B$6:$B$20,$A90,'S4'!$E$6:$E$20,"Ambos")+SUMIFS('S5'!$I$6:$I$20,'S5'!$B$6:$B$20,$A90,'S5'!$E$6:$E$20,"Víctor")+SUMIFS('S5'!$I$6:$I$20,'S5'!$B$6:$B$20,$A90,'S5'!$E$6:$E$20,"Ambos")+SUMIFS('S6'!$I$6:$I$17,'S6'!$B$6:$B$17,$A90,'S6'!$E$6:$E$17,"Víctor")+SUMIFS('S6'!$I$6:$I$17,'S6'!$B$6:$B$17,$A90,'S6'!$E$6:$E$17,"Ambos")+SUMIFS('S7'!$I$6:$I$19,'S7'!$B$6:$B$19,$A90,'S7'!$E$6:$E$19,"Víctor")+SUMIFS('S7'!$I$6:$I$19,'S7'!$B$6:$B$19,$A90,'S7'!$E$6:$E$19,"Ambos")+SUMIFS('S8'!$I$6:$I$23,'S8'!$B$6:$B$23,$A90,'S8'!$E$6:$E$23,"Víctor")+SUMIFS('S8'!$I$6:$I$23,'S8'!$B$6:$B$23,$A90,'S8'!$E$6:$E$23,"Ambos")+SUMIFS('S9'!$I$6:$I$15,'S9'!$B$6:$B$15,$A90,'S9'!$E$6:$E$15,"Víctor")+SUMIFS('S9'!$I$6:$I$15,'S9'!$B$6:$B$15,$A90,'S9'!$E$6:$E$15,"Ambos")+SUMIFS('S10'!$I$6:$I$13,'S10'!$B$6:$B$13,$A90,'S10'!$E$6:$E$13,"Víctor")+SUMIFS('S10'!$I$6:$I$13,'S10'!$B$6:$B$13,$A90,'S10'!$E$6:$E$13,"Ambos")+SUMIFS('Holgura'!$I$6:$I$11,'Holgura'!$B$6:$B$11,$A90,'Holgura'!$E$6:$E$11,"Víctor")+SUMIFS('Holgura'!$I$6:$I$11,'Holgura'!$B$6:$B$11,$A90,'Holgura'!$E$6:$E$11,"Ambos")+SUMIFS('Entrega'!$I$6:$I$9,'Entrega'!$B$6:$B$9,$A90,'Entrega'!$E$6:$E$9,"Víctor")+SUMIFS('Entrega'!$I$6:$I$9,'Entrega'!$B$6:$B$9,$A90,'Entrega'!$E$6:$E$9,"Ambos")+SUMIFS('Defensa'!$I$6:$I$10,'Defensa'!$B$6:$B$10,$A90,'Defensa'!$E$6:$E$10,"Víctor")+SUMIFS('Defensa'!$I$6:$I$10,'Defensa'!$B$6:$B$10,$A90,'Defensa'!$E$6:$E$10,"Ambos")</f>
+        <f>SUMIFS('S1'!$I$6:$I$32,'S1'!$B$6:$B$32,$A90,'S1'!$E$6:$E$32,"Víctor")+SUMIFS('S1'!$I$6:$I$32,'S1'!$B$6:$B$32,$A90,'S1'!$E$6:$E$32,"Ambos")+SUMIFS('S2'!$I$6:$I$23,'S2'!$B$6:$B$23,$A90,'S2'!$E$6:$E$23,"Víctor")+SUMIFS('S2'!$I$6:$I$23,'S2'!$B$6:$B$23,$A90,'S2'!$E$6:$E$23,"Ambos")+SUMIFS('S3'!$I$6:$I$24,'S3'!$B$6:$B$24,$A90,'S3'!$E$6:$E$24,"Víctor")+SUMIFS('S3'!$I$6:$I$24,'S3'!$B$6:$B$24,$A90,'S3'!$E$6:$E$24,"Ambos")+SUMIFS('S4'!$I$6:$I$22,'S4'!$B$6:$B$22,$A90,'S4'!$E$6:$E$22,"Víctor")+SUMIFS('S4'!$I$6:$I$22,'S4'!$B$6:$B$22,$A90,'S4'!$E$6:$E$22,"Ambos")+SUMIFS('S5'!$I$6:$I$20,'S5'!$B$6:$B$20,$A90,'S5'!$E$6:$E$20,"Víctor")+SUMIFS('S5'!$I$6:$I$20,'S5'!$B$6:$B$20,$A90,'S5'!$E$6:$E$20,"Ambos")+SUMIFS('S6'!$I$6:$I$17,'S6'!$B$6:$B$17,$A90,'S6'!$E$6:$E$17,"Víctor")+SUMIFS('S6'!$I$6:$I$17,'S6'!$B$6:$B$17,$A90,'S6'!$E$6:$E$17,"Ambos")+SUMIFS('S7'!$I$6:$I$19,'S7'!$B$6:$B$19,$A90,'S7'!$E$6:$E$19,"Víctor")+SUMIFS('S7'!$I$6:$I$19,'S7'!$B$6:$B$19,$A90,'S7'!$E$6:$E$19,"Ambos")+SUMIFS('S8'!$I$6:$I$23,'S8'!$B$6:$B$23,$A90,'S8'!$E$6:$E$23,"Víctor")+SUMIFS('S8'!$I$6:$I$23,'S8'!$B$6:$B$23,$A90,'S8'!$E$6:$E$23,"Ambos")+SUMIFS('S9'!$I$6:$I$15,'S9'!$B$6:$B$15,$A90,'S9'!$E$6:$E$15,"Víctor")+SUMIFS('S9'!$I$6:$I$15,'S9'!$B$6:$B$15,$A90,'S9'!$E$6:$E$15,"Ambos")+SUMIFS('S10'!$I$6:$I$13,'S10'!$B$6:$B$13,$A90,'S10'!$E$6:$E$13,"Víctor")+SUMIFS('S10'!$I$6:$I$13,'S10'!$B$6:$B$13,$A90,'S10'!$E$6:$E$13,"Ambos")+SUMIFS('Holgura'!$I$6:$I$11,'Holgura'!$B$6:$B$11,$A90,'Holgura'!$E$6:$E$11,"Víctor")+SUMIFS('Holgura'!$I$6:$I$11,'Holgura'!$B$6:$B$11,$A90,'Holgura'!$E$6:$E$11,"Ambos")+SUMIFS('Entrega'!$I$6:$I$9,'Entrega'!$B$6:$B$9,$A90,'Entrega'!$E$6:$E$9,"Víctor")+SUMIFS('Entrega'!$I$6:$I$9,'Entrega'!$B$6:$B$9,$A90,'Entrega'!$E$6:$E$9,"Ambos")+SUMIFS('Defensa'!$I$6:$I$10,'Defensa'!$B$6:$B$10,$A90,'Defensa'!$E$6:$E$10,"Víctor")+SUMIFS('Defensa'!$I$6:$I$10,'Defensa'!$B$6:$B$10,$A90,'Defensa'!$E$6:$E$10,"Ambos")</f>
         <v/>
       </c>
       <c r="E90" s="21">
-        <f>SUMIFS('S1'!$I$6:$I$32,'S1'!$B$6:$B$32,$A90,'S1'!$E$6:$E$32,"Diego")+SUMIFS('S1'!$I$6:$I$32,'S1'!$B$6:$B$32,$A90,'S1'!$E$6:$E$32,"Ambos")+SUMIFS('S2'!$I$6:$I$23,'S2'!$B$6:$B$23,$A90,'S2'!$E$6:$E$23,"Diego")+SUMIFS('S2'!$I$6:$I$23,'S2'!$B$6:$B$23,$A90,'S2'!$E$6:$E$23,"Ambos")+SUMIFS('S3'!$I$6:$I$19,'S3'!$B$6:$B$19,$A90,'S3'!$E$6:$E$19,"Diego")+SUMIFS('S3'!$I$6:$I$19,'S3'!$B$6:$B$19,$A90,'S3'!$E$6:$E$19,"Ambos")+SUMIFS('S4'!$I$6:$I$20,'S4'!$B$6:$B$20,$A90,'S4'!$E$6:$E$20,"Diego")+SUMIFS('S4'!$I$6:$I$20,'S4'!$B$6:$B$20,$A90,'S4'!$E$6:$E$20,"Ambos")+SUMIFS('S5'!$I$6:$I$20,'S5'!$B$6:$B$20,$A90,'S5'!$E$6:$E$20,"Diego")+SUMIFS('S5'!$I$6:$I$20,'S5'!$B$6:$B$20,$A90,'S5'!$E$6:$E$20,"Ambos")+SUMIFS('S6'!$I$6:$I$17,'S6'!$B$6:$B$17,$A90,'S6'!$E$6:$E$17,"Diego")+SUMIFS('S6'!$I$6:$I$17,'S6'!$B$6:$B$17,$A90,'S6'!$E$6:$E$17,"Ambos")+SUMIFS('S7'!$I$6:$I$19,'S7'!$B$6:$B$19,$A90,'S7'!$E$6:$E$19,"Diego")+SUMIFS('S7'!$I$6:$I$19,'S7'!$B$6:$B$19,$A90,'S7'!$E$6:$E$19,"Ambos")+SUMIFS('S8'!$I$6:$I$23,'S8'!$B$6:$B$23,$A90,'S8'!$E$6:$E$23,"Diego")+SUMIFS('S8'!$I$6:$I$23,'S8'!$B$6:$B$23,$A90,'S8'!$E$6:$E$23,"Ambos")+SUMIFS('S9'!$I$6:$I$15,'S9'!$B$6:$B$15,$A90,'S9'!$E$6:$E$15,"Diego")+SUMIFS('S9'!$I$6:$I$15,'S9'!$B$6:$B$15,$A90,'S9'!$E$6:$E$15,"Ambos")+SUMIFS('S10'!$I$6:$I$13,'S10'!$B$6:$B$13,$A90,'S10'!$E$6:$E$13,"Diego")+SUMIFS('S10'!$I$6:$I$13,'S10'!$B$6:$B$13,$A90,'S10'!$E$6:$E$13,"Ambos")+SUMIFS('Holgura'!$I$6:$I$11,'Holgura'!$B$6:$B$11,$A90,'Holgura'!$E$6:$E$11,"Diego")+SUMIFS('Holgura'!$I$6:$I$11,'Holgura'!$B$6:$B$11,$A90,'Holgura'!$E$6:$E$11,"Ambos")+SUMIFS('Entrega'!$I$6:$I$9,'Entrega'!$B$6:$B$9,$A90,'Entrega'!$E$6:$E$9,"Diego")+SUMIFS('Entrega'!$I$6:$I$9,'Entrega'!$B$6:$B$9,$A90,'Entrega'!$E$6:$E$9,"Ambos")+SUMIFS('Defensa'!$I$6:$I$10,'Defensa'!$B$6:$B$10,$A90,'Defensa'!$E$6:$E$10,"Diego")+SUMIFS('Defensa'!$I$6:$I$10,'Defensa'!$B$6:$B$10,$A90,'Defensa'!$E$6:$E$10,"Ambos")</f>
+        <f>SUMIFS('S1'!$I$6:$I$32,'S1'!$B$6:$B$32,$A90,'S1'!$E$6:$E$32,"Diego")+SUMIFS('S1'!$I$6:$I$32,'S1'!$B$6:$B$32,$A90,'S1'!$E$6:$E$32,"Ambos")+SUMIFS('S2'!$I$6:$I$23,'S2'!$B$6:$B$23,$A90,'S2'!$E$6:$E$23,"Diego")+SUMIFS('S2'!$I$6:$I$23,'S2'!$B$6:$B$23,$A90,'S2'!$E$6:$E$23,"Ambos")+SUMIFS('S3'!$I$6:$I$24,'S3'!$B$6:$B$24,$A90,'S3'!$E$6:$E$24,"Diego")+SUMIFS('S3'!$I$6:$I$24,'S3'!$B$6:$B$24,$A90,'S3'!$E$6:$E$24,"Ambos")+SUMIFS('S4'!$I$6:$I$22,'S4'!$B$6:$B$22,$A90,'S4'!$E$6:$E$22,"Diego")+SUMIFS('S4'!$I$6:$I$22,'S4'!$B$6:$B$22,$A90,'S4'!$E$6:$E$22,"Ambos")+SUMIFS('S5'!$I$6:$I$20,'S5'!$B$6:$B$20,$A90,'S5'!$E$6:$E$20,"Diego")+SUMIFS('S5'!$I$6:$I$20,'S5'!$B$6:$B$20,$A90,'S5'!$E$6:$E$20,"Ambos")+SUMIFS('S6'!$I$6:$I$17,'S6'!$B$6:$B$17,$A90,'S6'!$E$6:$E$17,"Diego")+SUMIFS('S6'!$I$6:$I$17,'S6'!$B$6:$B$17,$A90,'S6'!$E$6:$E$17,"Ambos")+SUMIFS('S7'!$I$6:$I$19,'S7'!$B$6:$B$19,$A90,'S7'!$E$6:$E$19,"Diego")+SUMIFS('S7'!$I$6:$I$19,'S7'!$B$6:$B$19,$A90,'S7'!$E$6:$E$19,"Ambos")+SUMIFS('S8'!$I$6:$I$23,'S8'!$B$6:$B$23,$A90,'S8'!$E$6:$E$23,"Diego")+SUMIFS('S8'!$I$6:$I$23,'S8'!$B$6:$B$23,$A90,'S8'!$E$6:$E$23,"Ambos")+SUMIFS('S9'!$I$6:$I$15,'S9'!$B$6:$B$15,$A90,'S9'!$E$6:$E$15,"Diego")+SUMIFS('S9'!$I$6:$I$15,'S9'!$B$6:$B$15,$A90,'S9'!$E$6:$E$15,"Ambos")+SUMIFS('S10'!$I$6:$I$13,'S10'!$B$6:$B$13,$A90,'S10'!$E$6:$E$13,"Diego")+SUMIFS('S10'!$I$6:$I$13,'S10'!$B$6:$B$13,$A90,'S10'!$E$6:$E$13,"Ambos")+SUMIFS('Holgura'!$I$6:$I$11,'Holgura'!$B$6:$B$11,$A90,'Holgura'!$E$6:$E$11,"Diego")+SUMIFS('Holgura'!$I$6:$I$11,'Holgura'!$B$6:$B$11,$A90,'Holgura'!$E$6:$E$11,"Ambos")+SUMIFS('Entrega'!$I$6:$I$9,'Entrega'!$B$6:$B$9,$A90,'Entrega'!$E$6:$E$9,"Diego")+SUMIFS('Entrega'!$I$6:$I$9,'Entrega'!$B$6:$B$9,$A90,'Entrega'!$E$6:$E$9,"Ambos")+SUMIFS('Defensa'!$I$6:$I$10,'Defensa'!$B$6:$B$10,$A90,'Defensa'!$E$6:$E$10,"Diego")+SUMIFS('Defensa'!$I$6:$I$10,'Defensa'!$B$6:$B$10,$A90,'Defensa'!$E$6:$E$10,"Ambos")</f>
         <v/>
       </c>
       <c r="F90" s="21">
-        <f>COUNTIFS('S1'!$B$6:$B$32,$A90,'S1'!$E$6:$E$32,"Víctor")+COUNTIFS('S1'!$B$6:$B$32,$A90,'S1'!$E$6:$E$32,"Ambos")+COUNTIFS('S2'!$B$6:$B$23,$A90,'S2'!$E$6:$E$23,"Víctor")+COUNTIFS('S2'!$B$6:$B$23,$A90,'S2'!$E$6:$E$23,"Ambos")+COUNTIFS('S3'!$B$6:$B$19,$A90,'S3'!$E$6:$E$19,"Víctor")+COUNTIFS('S3'!$B$6:$B$19,$A90,'S3'!$E$6:$E$19,"Ambos")+COUNTIFS('S4'!$B$6:$B$20,$A90,'S4'!$E$6:$E$20,"Víctor")+COUNTIFS('S4'!$B$6:$B$20,$A90,'S4'!$E$6:$E$20,"Ambos")+COUNTIFS('S5'!$B$6:$B$20,$A90,'S5'!$E$6:$E$20,"Víctor")+COUNTIFS('S5'!$B$6:$B$20,$A90,'S5'!$E$6:$E$20,"Ambos")+COUNTIFS('S6'!$B$6:$B$17,$A90,'S6'!$E$6:$E$17,"Víctor")+COUNTIFS('S6'!$B$6:$B$17,$A90,'S6'!$E$6:$E$17,"Ambos")+COUNTIFS('S7'!$B$6:$B$19,$A90,'S7'!$E$6:$E$19,"Víctor")+COUNTIFS('S7'!$B$6:$B$19,$A90,'S7'!$E$6:$E$19,"Ambos")+COUNTIFS('S8'!$B$6:$B$23,$A90,'S8'!$E$6:$E$23,"Víctor")+COUNTIFS('S8'!$B$6:$B$23,$A90,'S8'!$E$6:$E$23,"Ambos")+COUNTIFS('S9'!$B$6:$B$15,$A90,'S9'!$E$6:$E$15,"Víctor")+COUNTIFS('S9'!$B$6:$B$15,$A90,'S9'!$E$6:$E$15,"Ambos")+COUNTIFS('S10'!$B$6:$B$13,$A90,'S10'!$E$6:$E$13,"Víctor")+COUNTIFS('S10'!$B$6:$B$13,$A90,'S10'!$E$6:$E$13,"Ambos")+COUNTIFS('Holgura'!$B$6:$B$11,$A90,'Holgura'!$E$6:$E$11,"Víctor")+COUNTIFS('Holgura'!$B$6:$B$11,$A90,'Holgura'!$E$6:$E$11,"Ambos")+COUNTIFS('Entrega'!$B$6:$B$9,$A90,'Entrega'!$E$6:$E$9,"Víctor")+COUNTIFS('Entrega'!$B$6:$B$9,$A90,'Entrega'!$E$6:$E$9,"Ambos")+COUNTIFS('Defensa'!$B$6:$B$10,$A90,'Defensa'!$E$6:$E$10,"Víctor")+COUNTIFS('Defensa'!$B$6:$B$10,$A90,'Defensa'!$E$6:$E$10,"Ambos")</f>
+        <f>COUNTIFS('S1'!$B$6:$B$32,$A90,'S1'!$E$6:$E$32,"Víctor")+COUNTIFS('S1'!$B$6:$B$32,$A90,'S1'!$E$6:$E$32,"Ambos")+COUNTIFS('S2'!$B$6:$B$23,$A90,'S2'!$E$6:$E$23,"Víctor")+COUNTIFS('S2'!$B$6:$B$23,$A90,'S2'!$E$6:$E$23,"Ambos")+COUNTIFS('S3'!$B$6:$B$24,$A90,'S3'!$E$6:$E$24,"Víctor")+COUNTIFS('S3'!$B$6:$B$24,$A90,'S3'!$E$6:$E$24,"Ambos")+COUNTIFS('S4'!$B$6:$B$22,$A90,'S4'!$E$6:$E$22,"Víctor")+COUNTIFS('S4'!$B$6:$B$22,$A90,'S4'!$E$6:$E$22,"Ambos")+COUNTIFS('S5'!$B$6:$B$20,$A90,'S5'!$E$6:$E$20,"Víctor")+COUNTIFS('S5'!$B$6:$B$20,$A90,'S5'!$E$6:$E$20,"Ambos")+COUNTIFS('S6'!$B$6:$B$17,$A90,'S6'!$E$6:$E$17,"Víctor")+COUNTIFS('S6'!$B$6:$B$17,$A90,'S6'!$E$6:$E$17,"Ambos")+COUNTIFS('S7'!$B$6:$B$19,$A90,'S7'!$E$6:$E$19,"Víctor")+COUNTIFS('S7'!$B$6:$B$19,$A90,'S7'!$E$6:$E$19,"Ambos")+COUNTIFS('S8'!$B$6:$B$23,$A90,'S8'!$E$6:$E$23,"Víctor")+COUNTIFS('S8'!$B$6:$B$23,$A90,'S8'!$E$6:$E$23,"Ambos")+COUNTIFS('S9'!$B$6:$B$15,$A90,'S9'!$E$6:$E$15,"Víctor")+COUNTIFS('S9'!$B$6:$B$15,$A90,'S9'!$E$6:$E$15,"Ambos")+COUNTIFS('S10'!$B$6:$B$13,$A90,'S10'!$E$6:$E$13,"Víctor")+COUNTIFS('S10'!$B$6:$B$13,$A90,'S10'!$E$6:$E$13,"Ambos")+COUNTIFS('Holgura'!$B$6:$B$11,$A90,'Holgura'!$E$6:$E$11,"Víctor")+COUNTIFS('Holgura'!$B$6:$B$11,$A90,'Holgura'!$E$6:$E$11,"Ambos")+COUNTIFS('Entrega'!$B$6:$B$9,$A90,'Entrega'!$E$6:$E$9,"Víctor")+COUNTIFS('Entrega'!$B$6:$B$9,$A90,'Entrega'!$E$6:$E$9,"Ambos")+COUNTIFS('Defensa'!$B$6:$B$10,$A90,'Defensa'!$E$6:$E$10,"Víctor")+COUNTIFS('Defensa'!$B$6:$B$10,$A90,'Defensa'!$E$6:$E$10,"Ambos")</f>
         <v/>
       </c>
       <c r="G90" s="21">
-        <f>COUNTIFS('S1'!$B$6:$B$32,$A90,'S1'!$E$6:$E$32,"Diego")+COUNTIFS('S1'!$B$6:$B$32,$A90,'S1'!$E$6:$E$32,"Ambos")+COUNTIFS('S2'!$B$6:$B$23,$A90,'S2'!$E$6:$E$23,"Diego")+COUNTIFS('S2'!$B$6:$B$23,$A90,'S2'!$E$6:$E$23,"Ambos")+COUNTIFS('S3'!$B$6:$B$19,$A90,'S3'!$E$6:$E$19,"Diego")+COUNTIFS('S3'!$B$6:$B$19,$A90,'S3'!$E$6:$E$19,"Ambos")+COUNTIFS('S4'!$B$6:$B$20,$A90,'S4'!$E$6:$E$20,"Diego")+COUNTIFS('S4'!$B$6:$B$20,$A90,'S4'!$E$6:$E$20,"Ambos")+COUNTIFS('S5'!$B$6:$B$20,$A90,'S5'!$E$6:$E$20,"Diego")+COUNTIFS('S5'!$B$6:$B$20,$A90,'S5'!$E$6:$E$20,"Ambos")+COUNTIFS('S6'!$B$6:$B$17,$A90,'S6'!$E$6:$E$17,"Diego")+COUNTIFS('S6'!$B$6:$B$17,$A90,'S6'!$E$6:$E$17,"Ambos")+COUNTIFS('S7'!$B$6:$B$19,$A90,'S7'!$E$6:$E$19,"Diego")+COUNTIFS('S7'!$B$6:$B$19,$A90,'S7'!$E$6:$E$19,"Ambos")+COUNTIFS('S8'!$B$6:$B$23,$A90,'S8'!$E$6:$E$23,"Diego")+COUNTIFS('S8'!$B$6:$B$23,$A90,'S8'!$E$6:$E$23,"Ambos")+COUNTIFS('S9'!$B$6:$B$15,$A90,'S9'!$E$6:$E$15,"Diego")+COUNTIFS('S9'!$B$6:$B$15,$A90,'S9'!$E$6:$E$15,"Ambos")+COUNTIFS('S10'!$B$6:$B$13,$A90,'S10'!$E$6:$E$13,"Diego")+COUNTIFS('S10'!$B$6:$B$13,$A90,'S10'!$E$6:$E$13,"Ambos")+COUNTIFS('Holgura'!$B$6:$B$11,$A90,'Holgura'!$E$6:$E$11,"Diego")+COUNTIFS('Holgura'!$B$6:$B$11,$A90,'Holgura'!$E$6:$E$11,"Ambos")+COUNTIFS('Entrega'!$B$6:$B$9,$A90,'Entrega'!$E$6:$E$9,"Diego")+COUNTIFS('Entrega'!$B$6:$B$9,$A90,'Entrega'!$E$6:$E$9,"Ambos")+COUNTIFS('Defensa'!$B$6:$B$10,$A90,'Defensa'!$E$6:$E$10,"Diego")+COUNTIFS('Defensa'!$B$6:$B$10,$A90,'Defensa'!$E$6:$E$10,"Ambos")</f>
+        <f>COUNTIFS('S1'!$B$6:$B$32,$A90,'S1'!$E$6:$E$32,"Diego")+COUNTIFS('S1'!$B$6:$B$32,$A90,'S1'!$E$6:$E$32,"Ambos")+COUNTIFS('S2'!$B$6:$B$23,$A90,'S2'!$E$6:$E$23,"Diego")+COUNTIFS('S2'!$B$6:$B$23,$A90,'S2'!$E$6:$E$23,"Ambos")+COUNTIFS('S3'!$B$6:$B$24,$A90,'S3'!$E$6:$E$24,"Diego")+COUNTIFS('S3'!$B$6:$B$24,$A90,'S3'!$E$6:$E$24,"Ambos")+COUNTIFS('S4'!$B$6:$B$22,$A90,'S4'!$E$6:$E$22,"Diego")+COUNTIFS('S4'!$B$6:$B$22,$A90,'S4'!$E$6:$E$22,"Ambos")+COUNTIFS('S5'!$B$6:$B$20,$A90,'S5'!$E$6:$E$20,"Diego")+COUNTIFS('S5'!$B$6:$B$20,$A90,'S5'!$E$6:$E$20,"Ambos")+COUNTIFS('S6'!$B$6:$B$17,$A90,'S6'!$E$6:$E$17,"Diego")+COUNTIFS('S6'!$B$6:$B$17,$A90,'S6'!$E$6:$E$17,"Ambos")+COUNTIFS('S7'!$B$6:$B$19,$A90,'S7'!$E$6:$E$19,"Diego")+COUNTIFS('S7'!$B$6:$B$19,$A90,'S7'!$E$6:$E$19,"Ambos")+COUNTIFS('S8'!$B$6:$B$23,$A90,'S8'!$E$6:$E$23,"Diego")+COUNTIFS('S8'!$B$6:$B$23,$A90,'S8'!$E$6:$E$23,"Ambos")+COUNTIFS('S9'!$B$6:$B$15,$A90,'S9'!$E$6:$E$15,"Diego")+COUNTIFS('S9'!$B$6:$B$15,$A90,'S9'!$E$6:$E$15,"Ambos")+COUNTIFS('S10'!$B$6:$B$13,$A90,'S10'!$E$6:$E$13,"Diego")+COUNTIFS('S10'!$B$6:$B$13,$A90,'S10'!$E$6:$E$13,"Ambos")+COUNTIFS('Holgura'!$B$6:$B$11,$A90,'Holgura'!$E$6:$E$11,"Diego")+COUNTIFS('Holgura'!$B$6:$B$11,$A90,'Holgura'!$E$6:$E$11,"Ambos")+COUNTIFS('Entrega'!$B$6:$B$9,$A90,'Entrega'!$E$6:$E$9,"Diego")+COUNTIFS('Entrega'!$B$6:$B$9,$A90,'Entrega'!$E$6:$E$9,"Ambos")+COUNTIFS('Defensa'!$B$6:$B$10,$A90,'Defensa'!$E$6:$E$10,"Diego")+COUNTIFS('Defensa'!$B$6:$B$10,$A90,'Defensa'!$E$6:$E$10,"Ambos")</f>
         <v/>
       </c>
     </row>
@@ -11174,19 +11195,19 @@
         <v/>
       </c>
       <c r="D91" s="21">
-        <f>SUMIFS('S1'!$I$6:$I$32,'S1'!$B$6:$B$32,$A91,'S1'!$E$6:$E$32,"Víctor")+SUMIFS('S1'!$I$6:$I$32,'S1'!$B$6:$B$32,$A91,'S1'!$E$6:$E$32,"Ambos")+SUMIFS('S2'!$I$6:$I$23,'S2'!$B$6:$B$23,$A91,'S2'!$E$6:$E$23,"Víctor")+SUMIFS('S2'!$I$6:$I$23,'S2'!$B$6:$B$23,$A91,'S2'!$E$6:$E$23,"Ambos")+SUMIFS('S3'!$I$6:$I$19,'S3'!$B$6:$B$19,$A91,'S3'!$E$6:$E$19,"Víctor")+SUMIFS('S3'!$I$6:$I$19,'S3'!$B$6:$B$19,$A91,'S3'!$E$6:$E$19,"Ambos")+SUMIFS('S4'!$I$6:$I$20,'S4'!$B$6:$B$20,$A91,'S4'!$E$6:$E$20,"Víctor")+SUMIFS('S4'!$I$6:$I$20,'S4'!$B$6:$B$20,$A91,'S4'!$E$6:$E$20,"Ambos")+SUMIFS('S5'!$I$6:$I$20,'S5'!$B$6:$B$20,$A91,'S5'!$E$6:$E$20,"Víctor")+SUMIFS('S5'!$I$6:$I$20,'S5'!$B$6:$B$20,$A91,'S5'!$E$6:$E$20,"Ambos")+SUMIFS('S6'!$I$6:$I$17,'S6'!$B$6:$B$17,$A91,'S6'!$E$6:$E$17,"Víctor")+SUMIFS('S6'!$I$6:$I$17,'S6'!$B$6:$B$17,$A91,'S6'!$E$6:$E$17,"Ambos")+SUMIFS('S7'!$I$6:$I$19,'S7'!$B$6:$B$19,$A91,'S7'!$E$6:$E$19,"Víctor")+SUMIFS('S7'!$I$6:$I$19,'S7'!$B$6:$B$19,$A91,'S7'!$E$6:$E$19,"Ambos")+SUMIFS('S8'!$I$6:$I$23,'S8'!$B$6:$B$23,$A91,'S8'!$E$6:$E$23,"Víctor")+SUMIFS('S8'!$I$6:$I$23,'S8'!$B$6:$B$23,$A91,'S8'!$E$6:$E$23,"Ambos")+SUMIFS('S9'!$I$6:$I$15,'S9'!$B$6:$B$15,$A91,'S9'!$E$6:$E$15,"Víctor")+SUMIFS('S9'!$I$6:$I$15,'S9'!$B$6:$B$15,$A91,'S9'!$E$6:$E$15,"Ambos")+SUMIFS('S10'!$I$6:$I$13,'S10'!$B$6:$B$13,$A91,'S10'!$E$6:$E$13,"Víctor")+SUMIFS('S10'!$I$6:$I$13,'S10'!$B$6:$B$13,$A91,'S10'!$E$6:$E$13,"Ambos")+SUMIFS('Holgura'!$I$6:$I$11,'Holgura'!$B$6:$B$11,$A91,'Holgura'!$E$6:$E$11,"Víctor")+SUMIFS('Holgura'!$I$6:$I$11,'Holgura'!$B$6:$B$11,$A91,'Holgura'!$E$6:$E$11,"Ambos")+SUMIFS('Entrega'!$I$6:$I$9,'Entrega'!$B$6:$B$9,$A91,'Entrega'!$E$6:$E$9,"Víctor")+SUMIFS('Entrega'!$I$6:$I$9,'Entrega'!$B$6:$B$9,$A91,'Entrega'!$E$6:$E$9,"Ambos")+SUMIFS('Defensa'!$I$6:$I$10,'Defensa'!$B$6:$B$10,$A91,'Defensa'!$E$6:$E$10,"Víctor")+SUMIFS('Defensa'!$I$6:$I$10,'Defensa'!$B$6:$B$10,$A91,'Defensa'!$E$6:$E$10,"Ambos")</f>
+        <f>SUMIFS('S1'!$I$6:$I$32,'S1'!$B$6:$B$32,$A91,'S1'!$E$6:$E$32,"Víctor")+SUMIFS('S1'!$I$6:$I$32,'S1'!$B$6:$B$32,$A91,'S1'!$E$6:$E$32,"Ambos")+SUMIFS('S2'!$I$6:$I$23,'S2'!$B$6:$B$23,$A91,'S2'!$E$6:$E$23,"Víctor")+SUMIFS('S2'!$I$6:$I$23,'S2'!$B$6:$B$23,$A91,'S2'!$E$6:$E$23,"Ambos")+SUMIFS('S3'!$I$6:$I$24,'S3'!$B$6:$B$24,$A91,'S3'!$E$6:$E$24,"Víctor")+SUMIFS('S3'!$I$6:$I$24,'S3'!$B$6:$B$24,$A91,'S3'!$E$6:$E$24,"Ambos")+SUMIFS('S4'!$I$6:$I$22,'S4'!$B$6:$B$22,$A91,'S4'!$E$6:$E$22,"Víctor")+SUMIFS('S4'!$I$6:$I$22,'S4'!$B$6:$B$22,$A91,'S4'!$E$6:$E$22,"Ambos")+SUMIFS('S5'!$I$6:$I$20,'S5'!$B$6:$B$20,$A91,'S5'!$E$6:$E$20,"Víctor")+SUMIFS('S5'!$I$6:$I$20,'S5'!$B$6:$B$20,$A91,'S5'!$E$6:$E$20,"Ambos")+SUMIFS('S6'!$I$6:$I$17,'S6'!$B$6:$B$17,$A91,'S6'!$E$6:$E$17,"Víctor")+SUMIFS('S6'!$I$6:$I$17,'S6'!$B$6:$B$17,$A91,'S6'!$E$6:$E$17,"Ambos")+SUMIFS('S7'!$I$6:$I$19,'S7'!$B$6:$B$19,$A91,'S7'!$E$6:$E$19,"Víctor")+SUMIFS('S7'!$I$6:$I$19,'S7'!$B$6:$B$19,$A91,'S7'!$E$6:$E$19,"Ambos")+SUMIFS('S8'!$I$6:$I$23,'S8'!$B$6:$B$23,$A91,'S8'!$E$6:$E$23,"Víctor")+SUMIFS('S8'!$I$6:$I$23,'S8'!$B$6:$B$23,$A91,'S8'!$E$6:$E$23,"Ambos")+SUMIFS('S9'!$I$6:$I$15,'S9'!$B$6:$B$15,$A91,'S9'!$E$6:$E$15,"Víctor")+SUMIFS('S9'!$I$6:$I$15,'S9'!$B$6:$B$15,$A91,'S9'!$E$6:$E$15,"Ambos")+SUMIFS('S10'!$I$6:$I$13,'S10'!$B$6:$B$13,$A91,'S10'!$E$6:$E$13,"Víctor")+SUMIFS('S10'!$I$6:$I$13,'S10'!$B$6:$B$13,$A91,'S10'!$E$6:$E$13,"Ambos")+SUMIFS('Holgura'!$I$6:$I$11,'Holgura'!$B$6:$B$11,$A91,'Holgura'!$E$6:$E$11,"Víctor")+SUMIFS('Holgura'!$I$6:$I$11,'Holgura'!$B$6:$B$11,$A91,'Holgura'!$E$6:$E$11,"Ambos")+SUMIFS('Entrega'!$I$6:$I$9,'Entrega'!$B$6:$B$9,$A91,'Entrega'!$E$6:$E$9,"Víctor")+SUMIFS('Entrega'!$I$6:$I$9,'Entrega'!$B$6:$B$9,$A91,'Entrega'!$E$6:$E$9,"Ambos")+SUMIFS('Defensa'!$I$6:$I$10,'Defensa'!$B$6:$B$10,$A91,'Defensa'!$E$6:$E$10,"Víctor")+SUMIFS('Defensa'!$I$6:$I$10,'Defensa'!$B$6:$B$10,$A91,'Defensa'!$E$6:$E$10,"Ambos")</f>
         <v/>
       </c>
       <c r="E91" s="21">
-        <f>SUMIFS('S1'!$I$6:$I$32,'S1'!$B$6:$B$32,$A91,'S1'!$E$6:$E$32,"Diego")+SUMIFS('S1'!$I$6:$I$32,'S1'!$B$6:$B$32,$A91,'S1'!$E$6:$E$32,"Ambos")+SUMIFS('S2'!$I$6:$I$23,'S2'!$B$6:$B$23,$A91,'S2'!$E$6:$E$23,"Diego")+SUMIFS('S2'!$I$6:$I$23,'S2'!$B$6:$B$23,$A91,'S2'!$E$6:$E$23,"Ambos")+SUMIFS('S3'!$I$6:$I$19,'S3'!$B$6:$B$19,$A91,'S3'!$E$6:$E$19,"Diego")+SUMIFS('S3'!$I$6:$I$19,'S3'!$B$6:$B$19,$A91,'S3'!$E$6:$E$19,"Ambos")+SUMIFS('S4'!$I$6:$I$20,'S4'!$B$6:$B$20,$A91,'S4'!$E$6:$E$20,"Diego")+SUMIFS('S4'!$I$6:$I$20,'S4'!$B$6:$B$20,$A91,'S4'!$E$6:$E$20,"Ambos")+SUMIFS('S5'!$I$6:$I$20,'S5'!$B$6:$B$20,$A91,'S5'!$E$6:$E$20,"Diego")+SUMIFS('S5'!$I$6:$I$20,'S5'!$B$6:$B$20,$A91,'S5'!$E$6:$E$20,"Ambos")+SUMIFS('S6'!$I$6:$I$17,'S6'!$B$6:$B$17,$A91,'S6'!$E$6:$E$17,"Diego")+SUMIFS('S6'!$I$6:$I$17,'S6'!$B$6:$B$17,$A91,'S6'!$E$6:$E$17,"Ambos")+SUMIFS('S7'!$I$6:$I$19,'S7'!$B$6:$B$19,$A91,'S7'!$E$6:$E$19,"Diego")+SUMIFS('S7'!$I$6:$I$19,'S7'!$B$6:$B$19,$A91,'S7'!$E$6:$E$19,"Ambos")+SUMIFS('S8'!$I$6:$I$23,'S8'!$B$6:$B$23,$A91,'S8'!$E$6:$E$23,"Diego")+SUMIFS('S8'!$I$6:$I$23,'S8'!$B$6:$B$23,$A91,'S8'!$E$6:$E$23,"Ambos")+SUMIFS('S9'!$I$6:$I$15,'S9'!$B$6:$B$15,$A91,'S9'!$E$6:$E$15,"Diego")+SUMIFS('S9'!$I$6:$I$15,'S9'!$B$6:$B$15,$A91,'S9'!$E$6:$E$15,"Ambos")+SUMIFS('S10'!$I$6:$I$13,'S10'!$B$6:$B$13,$A91,'S10'!$E$6:$E$13,"Diego")+SUMIFS('S10'!$I$6:$I$13,'S10'!$B$6:$B$13,$A91,'S10'!$E$6:$E$13,"Ambos")+SUMIFS('Holgura'!$I$6:$I$11,'Holgura'!$B$6:$B$11,$A91,'Holgura'!$E$6:$E$11,"Diego")+SUMIFS('Holgura'!$I$6:$I$11,'Holgura'!$B$6:$B$11,$A91,'Holgura'!$E$6:$E$11,"Ambos")+SUMIFS('Entrega'!$I$6:$I$9,'Entrega'!$B$6:$B$9,$A91,'Entrega'!$E$6:$E$9,"Diego")+SUMIFS('Entrega'!$I$6:$I$9,'Entrega'!$B$6:$B$9,$A91,'Entrega'!$E$6:$E$9,"Ambos")+SUMIFS('Defensa'!$I$6:$I$10,'Defensa'!$B$6:$B$10,$A91,'Defensa'!$E$6:$E$10,"Diego")+SUMIFS('Defensa'!$I$6:$I$10,'Defensa'!$B$6:$B$10,$A91,'Defensa'!$E$6:$E$10,"Ambos")</f>
+        <f>SUMIFS('S1'!$I$6:$I$32,'S1'!$B$6:$B$32,$A91,'S1'!$E$6:$E$32,"Diego")+SUMIFS('S1'!$I$6:$I$32,'S1'!$B$6:$B$32,$A91,'S1'!$E$6:$E$32,"Ambos")+SUMIFS('S2'!$I$6:$I$23,'S2'!$B$6:$B$23,$A91,'S2'!$E$6:$E$23,"Diego")+SUMIFS('S2'!$I$6:$I$23,'S2'!$B$6:$B$23,$A91,'S2'!$E$6:$E$23,"Ambos")+SUMIFS('S3'!$I$6:$I$24,'S3'!$B$6:$B$24,$A91,'S3'!$E$6:$E$24,"Diego")+SUMIFS('S3'!$I$6:$I$24,'S3'!$B$6:$B$24,$A91,'S3'!$E$6:$E$24,"Ambos")+SUMIFS('S4'!$I$6:$I$22,'S4'!$B$6:$B$22,$A91,'S4'!$E$6:$E$22,"Diego")+SUMIFS('S4'!$I$6:$I$22,'S4'!$B$6:$B$22,$A91,'S4'!$E$6:$E$22,"Ambos")+SUMIFS('S5'!$I$6:$I$20,'S5'!$B$6:$B$20,$A91,'S5'!$E$6:$E$20,"Diego")+SUMIFS('S5'!$I$6:$I$20,'S5'!$B$6:$B$20,$A91,'S5'!$E$6:$E$20,"Ambos")+SUMIFS('S6'!$I$6:$I$17,'S6'!$B$6:$B$17,$A91,'S6'!$E$6:$E$17,"Diego")+SUMIFS('S6'!$I$6:$I$17,'S6'!$B$6:$B$17,$A91,'S6'!$E$6:$E$17,"Ambos")+SUMIFS('S7'!$I$6:$I$19,'S7'!$B$6:$B$19,$A91,'S7'!$E$6:$E$19,"Diego")+SUMIFS('S7'!$I$6:$I$19,'S7'!$B$6:$B$19,$A91,'S7'!$E$6:$E$19,"Ambos")+SUMIFS('S8'!$I$6:$I$23,'S8'!$B$6:$B$23,$A91,'S8'!$E$6:$E$23,"Diego")+SUMIFS('S8'!$I$6:$I$23,'S8'!$B$6:$B$23,$A91,'S8'!$E$6:$E$23,"Ambos")+SUMIFS('S9'!$I$6:$I$15,'S9'!$B$6:$B$15,$A91,'S9'!$E$6:$E$15,"Diego")+SUMIFS('S9'!$I$6:$I$15,'S9'!$B$6:$B$15,$A91,'S9'!$E$6:$E$15,"Ambos")+SUMIFS('S10'!$I$6:$I$13,'S10'!$B$6:$B$13,$A91,'S10'!$E$6:$E$13,"Diego")+SUMIFS('S10'!$I$6:$I$13,'S10'!$B$6:$B$13,$A91,'S10'!$E$6:$E$13,"Ambos")+SUMIFS('Holgura'!$I$6:$I$11,'Holgura'!$B$6:$B$11,$A91,'Holgura'!$E$6:$E$11,"Diego")+SUMIFS('Holgura'!$I$6:$I$11,'Holgura'!$B$6:$B$11,$A91,'Holgura'!$E$6:$E$11,"Ambos")+SUMIFS('Entrega'!$I$6:$I$9,'Entrega'!$B$6:$B$9,$A91,'Entrega'!$E$6:$E$9,"Diego")+SUMIFS('Entrega'!$I$6:$I$9,'Entrega'!$B$6:$B$9,$A91,'Entrega'!$E$6:$E$9,"Ambos")+SUMIFS('Defensa'!$I$6:$I$10,'Defensa'!$B$6:$B$10,$A91,'Defensa'!$E$6:$E$10,"Diego")+SUMIFS('Defensa'!$I$6:$I$10,'Defensa'!$B$6:$B$10,$A91,'Defensa'!$E$6:$E$10,"Ambos")</f>
         <v/>
       </c>
       <c r="F91" s="21">
-        <f>COUNTIFS('S1'!$B$6:$B$32,$A91,'S1'!$E$6:$E$32,"Víctor")+COUNTIFS('S1'!$B$6:$B$32,$A91,'S1'!$E$6:$E$32,"Ambos")+COUNTIFS('S2'!$B$6:$B$23,$A91,'S2'!$E$6:$E$23,"Víctor")+COUNTIFS('S2'!$B$6:$B$23,$A91,'S2'!$E$6:$E$23,"Ambos")+COUNTIFS('S3'!$B$6:$B$19,$A91,'S3'!$E$6:$E$19,"Víctor")+COUNTIFS('S3'!$B$6:$B$19,$A91,'S3'!$E$6:$E$19,"Ambos")+COUNTIFS('S4'!$B$6:$B$20,$A91,'S4'!$E$6:$E$20,"Víctor")+COUNTIFS('S4'!$B$6:$B$20,$A91,'S4'!$E$6:$E$20,"Ambos")+COUNTIFS('S5'!$B$6:$B$20,$A91,'S5'!$E$6:$E$20,"Víctor")+COUNTIFS('S5'!$B$6:$B$20,$A91,'S5'!$E$6:$E$20,"Ambos")+COUNTIFS('S6'!$B$6:$B$17,$A91,'S6'!$E$6:$E$17,"Víctor")+COUNTIFS('S6'!$B$6:$B$17,$A91,'S6'!$E$6:$E$17,"Ambos")+COUNTIFS('S7'!$B$6:$B$19,$A91,'S7'!$E$6:$E$19,"Víctor")+COUNTIFS('S7'!$B$6:$B$19,$A91,'S7'!$E$6:$E$19,"Ambos")+COUNTIFS('S8'!$B$6:$B$23,$A91,'S8'!$E$6:$E$23,"Víctor")+COUNTIFS('S8'!$B$6:$B$23,$A91,'S8'!$E$6:$E$23,"Ambos")+COUNTIFS('S9'!$B$6:$B$15,$A91,'S9'!$E$6:$E$15,"Víctor")+COUNTIFS('S9'!$B$6:$B$15,$A91,'S9'!$E$6:$E$15,"Ambos")+COUNTIFS('S10'!$B$6:$B$13,$A91,'S10'!$E$6:$E$13,"Víctor")+COUNTIFS('S10'!$B$6:$B$13,$A91,'S10'!$E$6:$E$13,"Ambos")+COUNTIFS('Holgura'!$B$6:$B$11,$A91,'Holgura'!$E$6:$E$11,"Víctor")+COUNTIFS('Holgura'!$B$6:$B$11,$A91,'Holgura'!$E$6:$E$11,"Ambos")+COUNTIFS('Entrega'!$B$6:$B$9,$A91,'Entrega'!$E$6:$E$9,"Víctor")+COUNTIFS('Entrega'!$B$6:$B$9,$A91,'Entrega'!$E$6:$E$9,"Ambos")+COUNTIFS('Defensa'!$B$6:$B$10,$A91,'Defensa'!$E$6:$E$10,"Víctor")+COUNTIFS('Defensa'!$B$6:$B$10,$A91,'Defensa'!$E$6:$E$10,"Ambos")</f>
+        <f>COUNTIFS('S1'!$B$6:$B$32,$A91,'S1'!$E$6:$E$32,"Víctor")+COUNTIFS('S1'!$B$6:$B$32,$A91,'S1'!$E$6:$E$32,"Ambos")+COUNTIFS('S2'!$B$6:$B$23,$A91,'S2'!$E$6:$E$23,"Víctor")+COUNTIFS('S2'!$B$6:$B$23,$A91,'S2'!$E$6:$E$23,"Ambos")+COUNTIFS('S3'!$B$6:$B$24,$A91,'S3'!$E$6:$E$24,"Víctor")+COUNTIFS('S3'!$B$6:$B$24,$A91,'S3'!$E$6:$E$24,"Ambos")+COUNTIFS('S4'!$B$6:$B$22,$A91,'S4'!$E$6:$E$22,"Víctor")+COUNTIFS('S4'!$B$6:$B$22,$A91,'S4'!$E$6:$E$22,"Ambos")+COUNTIFS('S5'!$B$6:$B$20,$A91,'S5'!$E$6:$E$20,"Víctor")+COUNTIFS('S5'!$B$6:$B$20,$A91,'S5'!$E$6:$E$20,"Ambos")+COUNTIFS('S6'!$B$6:$B$17,$A91,'S6'!$E$6:$E$17,"Víctor")+COUNTIFS('S6'!$B$6:$B$17,$A91,'S6'!$E$6:$E$17,"Ambos")+COUNTIFS('S7'!$B$6:$B$19,$A91,'S7'!$E$6:$E$19,"Víctor")+COUNTIFS('S7'!$B$6:$B$19,$A91,'S7'!$E$6:$E$19,"Ambos")+COUNTIFS('S8'!$B$6:$B$23,$A91,'S8'!$E$6:$E$23,"Víctor")+COUNTIFS('S8'!$B$6:$B$23,$A91,'S8'!$E$6:$E$23,"Ambos")+COUNTIFS('S9'!$B$6:$B$15,$A91,'S9'!$E$6:$E$15,"Víctor")+COUNTIFS('S9'!$B$6:$B$15,$A91,'S9'!$E$6:$E$15,"Ambos")+COUNTIFS('S10'!$B$6:$B$13,$A91,'S10'!$E$6:$E$13,"Víctor")+COUNTIFS('S10'!$B$6:$B$13,$A91,'S10'!$E$6:$E$13,"Ambos")+COUNTIFS('Holgura'!$B$6:$B$11,$A91,'Holgura'!$E$6:$E$11,"Víctor")+COUNTIFS('Holgura'!$B$6:$B$11,$A91,'Holgura'!$E$6:$E$11,"Ambos")+COUNTIFS('Entrega'!$B$6:$B$9,$A91,'Entrega'!$E$6:$E$9,"Víctor")+COUNTIFS('Entrega'!$B$6:$B$9,$A91,'Entrega'!$E$6:$E$9,"Ambos")+COUNTIFS('Defensa'!$B$6:$B$10,$A91,'Defensa'!$E$6:$E$10,"Víctor")+COUNTIFS('Defensa'!$B$6:$B$10,$A91,'Defensa'!$E$6:$E$10,"Ambos")</f>
         <v/>
       </c>
       <c r="G91" s="21">
-        <f>COUNTIFS('S1'!$B$6:$B$32,$A91,'S1'!$E$6:$E$32,"Diego")+COUNTIFS('S1'!$B$6:$B$32,$A91,'S1'!$E$6:$E$32,"Ambos")+COUNTIFS('S2'!$B$6:$B$23,$A91,'S2'!$E$6:$E$23,"Diego")+COUNTIFS('S2'!$B$6:$B$23,$A91,'S2'!$E$6:$E$23,"Ambos")+COUNTIFS('S3'!$B$6:$B$19,$A91,'S3'!$E$6:$E$19,"Diego")+COUNTIFS('S3'!$B$6:$B$19,$A91,'S3'!$E$6:$E$19,"Ambos")+COUNTIFS('S4'!$B$6:$B$20,$A91,'S4'!$E$6:$E$20,"Diego")+COUNTIFS('S4'!$B$6:$B$20,$A91,'S4'!$E$6:$E$20,"Ambos")+COUNTIFS('S5'!$B$6:$B$20,$A91,'S5'!$E$6:$E$20,"Diego")+COUNTIFS('S5'!$B$6:$B$20,$A91,'S5'!$E$6:$E$20,"Ambos")+COUNTIFS('S6'!$B$6:$B$17,$A91,'S6'!$E$6:$E$17,"Diego")+COUNTIFS('S6'!$B$6:$B$17,$A91,'S6'!$E$6:$E$17,"Ambos")+COUNTIFS('S7'!$B$6:$B$19,$A91,'S7'!$E$6:$E$19,"Diego")+COUNTIFS('S7'!$B$6:$B$19,$A91,'S7'!$E$6:$E$19,"Ambos")+COUNTIFS('S8'!$B$6:$B$23,$A91,'S8'!$E$6:$E$23,"Diego")+COUNTIFS('S8'!$B$6:$B$23,$A91,'S8'!$E$6:$E$23,"Ambos")+COUNTIFS('S9'!$B$6:$B$15,$A91,'S9'!$E$6:$E$15,"Diego")+COUNTIFS('S9'!$B$6:$B$15,$A91,'S9'!$E$6:$E$15,"Ambos")+COUNTIFS('S10'!$B$6:$B$13,$A91,'S10'!$E$6:$E$13,"Diego")+COUNTIFS('S10'!$B$6:$B$13,$A91,'S10'!$E$6:$E$13,"Ambos")+COUNTIFS('Holgura'!$B$6:$B$11,$A91,'Holgura'!$E$6:$E$11,"Diego")+COUNTIFS('Holgura'!$B$6:$B$11,$A91,'Holgura'!$E$6:$E$11,"Ambos")+COUNTIFS('Entrega'!$B$6:$B$9,$A91,'Entrega'!$E$6:$E$9,"Diego")+COUNTIFS('Entrega'!$B$6:$B$9,$A91,'Entrega'!$E$6:$E$9,"Ambos")+COUNTIFS('Defensa'!$B$6:$B$10,$A91,'Defensa'!$E$6:$E$10,"Diego")+COUNTIFS('Defensa'!$B$6:$B$10,$A91,'Defensa'!$E$6:$E$10,"Ambos")</f>
+        <f>COUNTIFS('S1'!$B$6:$B$32,$A91,'S1'!$E$6:$E$32,"Diego")+COUNTIFS('S1'!$B$6:$B$32,$A91,'S1'!$E$6:$E$32,"Ambos")+COUNTIFS('S2'!$B$6:$B$23,$A91,'S2'!$E$6:$E$23,"Diego")+COUNTIFS('S2'!$B$6:$B$23,$A91,'S2'!$E$6:$E$23,"Ambos")+COUNTIFS('S3'!$B$6:$B$24,$A91,'S3'!$E$6:$E$24,"Diego")+COUNTIFS('S3'!$B$6:$B$24,$A91,'S3'!$E$6:$E$24,"Ambos")+COUNTIFS('S4'!$B$6:$B$22,$A91,'S4'!$E$6:$E$22,"Diego")+COUNTIFS('S4'!$B$6:$B$22,$A91,'S4'!$E$6:$E$22,"Ambos")+COUNTIFS('S5'!$B$6:$B$20,$A91,'S5'!$E$6:$E$20,"Diego")+COUNTIFS('S5'!$B$6:$B$20,$A91,'S5'!$E$6:$E$20,"Ambos")+COUNTIFS('S6'!$B$6:$B$17,$A91,'S6'!$E$6:$E$17,"Diego")+COUNTIFS('S6'!$B$6:$B$17,$A91,'S6'!$E$6:$E$17,"Ambos")+COUNTIFS('S7'!$B$6:$B$19,$A91,'S7'!$E$6:$E$19,"Diego")+COUNTIFS('S7'!$B$6:$B$19,$A91,'S7'!$E$6:$E$19,"Ambos")+COUNTIFS('S8'!$B$6:$B$23,$A91,'S8'!$E$6:$E$23,"Diego")+COUNTIFS('S8'!$B$6:$B$23,$A91,'S8'!$E$6:$E$23,"Ambos")+COUNTIFS('S9'!$B$6:$B$15,$A91,'S9'!$E$6:$E$15,"Diego")+COUNTIFS('S9'!$B$6:$B$15,$A91,'S9'!$E$6:$E$15,"Ambos")+COUNTIFS('S10'!$B$6:$B$13,$A91,'S10'!$E$6:$E$13,"Diego")+COUNTIFS('S10'!$B$6:$B$13,$A91,'S10'!$E$6:$E$13,"Ambos")+COUNTIFS('Holgura'!$B$6:$B$11,$A91,'Holgura'!$E$6:$E$11,"Diego")+COUNTIFS('Holgura'!$B$6:$B$11,$A91,'Holgura'!$E$6:$E$11,"Ambos")+COUNTIFS('Entrega'!$B$6:$B$9,$A91,'Entrega'!$E$6:$E$9,"Diego")+COUNTIFS('Entrega'!$B$6:$B$9,$A91,'Entrega'!$E$6:$E$9,"Ambos")+COUNTIFS('Defensa'!$B$6:$B$10,$A91,'Defensa'!$E$6:$E$10,"Diego")+COUNTIFS('Defensa'!$B$6:$B$10,$A91,'Defensa'!$E$6:$E$10,"Ambos")</f>
         <v/>
       </c>
     </row>
@@ -11203,19 +11224,19 @@
         <v/>
       </c>
       <c r="D92" s="21">
-        <f>SUMIFS('S1'!$I$6:$I$32,'S1'!$B$6:$B$32,$A92,'S1'!$E$6:$E$32,"Víctor")+SUMIFS('S1'!$I$6:$I$32,'S1'!$B$6:$B$32,$A92,'S1'!$E$6:$E$32,"Ambos")+SUMIFS('S2'!$I$6:$I$23,'S2'!$B$6:$B$23,$A92,'S2'!$E$6:$E$23,"Víctor")+SUMIFS('S2'!$I$6:$I$23,'S2'!$B$6:$B$23,$A92,'S2'!$E$6:$E$23,"Ambos")+SUMIFS('S3'!$I$6:$I$19,'S3'!$B$6:$B$19,$A92,'S3'!$E$6:$E$19,"Víctor")+SUMIFS('S3'!$I$6:$I$19,'S3'!$B$6:$B$19,$A92,'S3'!$E$6:$E$19,"Ambos")+SUMIFS('S4'!$I$6:$I$20,'S4'!$B$6:$B$20,$A92,'S4'!$E$6:$E$20,"Víctor")+SUMIFS('S4'!$I$6:$I$20,'S4'!$B$6:$B$20,$A92,'S4'!$E$6:$E$20,"Ambos")+SUMIFS('S5'!$I$6:$I$20,'S5'!$B$6:$B$20,$A92,'S5'!$E$6:$E$20,"Víctor")+SUMIFS('S5'!$I$6:$I$20,'S5'!$B$6:$B$20,$A92,'S5'!$E$6:$E$20,"Ambos")+SUMIFS('S6'!$I$6:$I$17,'S6'!$B$6:$B$17,$A92,'S6'!$E$6:$E$17,"Víctor")+SUMIFS('S6'!$I$6:$I$17,'S6'!$B$6:$B$17,$A92,'S6'!$E$6:$E$17,"Ambos")+SUMIFS('S7'!$I$6:$I$19,'S7'!$B$6:$B$19,$A92,'S7'!$E$6:$E$19,"Víctor")+SUMIFS('S7'!$I$6:$I$19,'S7'!$B$6:$B$19,$A92,'S7'!$E$6:$E$19,"Ambos")+SUMIFS('S8'!$I$6:$I$23,'S8'!$B$6:$B$23,$A92,'S8'!$E$6:$E$23,"Víctor")+SUMIFS('S8'!$I$6:$I$23,'S8'!$B$6:$B$23,$A92,'S8'!$E$6:$E$23,"Ambos")+SUMIFS('S9'!$I$6:$I$15,'S9'!$B$6:$B$15,$A92,'S9'!$E$6:$E$15,"Víctor")+SUMIFS('S9'!$I$6:$I$15,'S9'!$B$6:$B$15,$A92,'S9'!$E$6:$E$15,"Ambos")+SUMIFS('S10'!$I$6:$I$13,'S10'!$B$6:$B$13,$A92,'S10'!$E$6:$E$13,"Víctor")+SUMIFS('S10'!$I$6:$I$13,'S10'!$B$6:$B$13,$A92,'S10'!$E$6:$E$13,"Ambos")+SUMIFS('Holgura'!$I$6:$I$11,'Holgura'!$B$6:$B$11,$A92,'Holgura'!$E$6:$E$11,"Víctor")+SUMIFS('Holgura'!$I$6:$I$11,'Holgura'!$B$6:$B$11,$A92,'Holgura'!$E$6:$E$11,"Ambos")+SUMIFS('Entrega'!$I$6:$I$9,'Entrega'!$B$6:$B$9,$A92,'Entrega'!$E$6:$E$9,"Víctor")+SUMIFS('Entrega'!$I$6:$I$9,'Entrega'!$B$6:$B$9,$A92,'Entrega'!$E$6:$E$9,"Ambos")+SUMIFS('Defensa'!$I$6:$I$10,'Defensa'!$B$6:$B$10,$A92,'Defensa'!$E$6:$E$10,"Víctor")+SUMIFS('Defensa'!$I$6:$I$10,'Defensa'!$B$6:$B$10,$A92,'Defensa'!$E$6:$E$10,"Ambos")</f>
+        <f>SUMIFS('S1'!$I$6:$I$32,'S1'!$B$6:$B$32,$A92,'S1'!$E$6:$E$32,"Víctor")+SUMIFS('S1'!$I$6:$I$32,'S1'!$B$6:$B$32,$A92,'S1'!$E$6:$E$32,"Ambos")+SUMIFS('S2'!$I$6:$I$23,'S2'!$B$6:$B$23,$A92,'S2'!$E$6:$E$23,"Víctor")+SUMIFS('S2'!$I$6:$I$23,'S2'!$B$6:$B$23,$A92,'S2'!$E$6:$E$23,"Ambos")+SUMIFS('S3'!$I$6:$I$24,'S3'!$B$6:$B$24,$A92,'S3'!$E$6:$E$24,"Víctor")+SUMIFS('S3'!$I$6:$I$24,'S3'!$B$6:$B$24,$A92,'S3'!$E$6:$E$24,"Ambos")+SUMIFS('S4'!$I$6:$I$22,'S4'!$B$6:$B$22,$A92,'S4'!$E$6:$E$22,"Víctor")+SUMIFS('S4'!$I$6:$I$22,'S4'!$B$6:$B$22,$A92,'S4'!$E$6:$E$22,"Ambos")+SUMIFS('S5'!$I$6:$I$20,'S5'!$B$6:$B$20,$A92,'S5'!$E$6:$E$20,"Víctor")+SUMIFS('S5'!$I$6:$I$20,'S5'!$B$6:$B$20,$A92,'S5'!$E$6:$E$20,"Ambos")+SUMIFS('S6'!$I$6:$I$17,'S6'!$B$6:$B$17,$A92,'S6'!$E$6:$E$17,"Víctor")+SUMIFS('S6'!$I$6:$I$17,'S6'!$B$6:$B$17,$A92,'S6'!$E$6:$E$17,"Ambos")+SUMIFS('S7'!$I$6:$I$19,'S7'!$B$6:$B$19,$A92,'S7'!$E$6:$E$19,"Víctor")+SUMIFS('S7'!$I$6:$I$19,'S7'!$B$6:$B$19,$A92,'S7'!$E$6:$E$19,"Ambos")+SUMIFS('S8'!$I$6:$I$23,'S8'!$B$6:$B$23,$A92,'S8'!$E$6:$E$23,"Víctor")+SUMIFS('S8'!$I$6:$I$23,'S8'!$B$6:$B$23,$A92,'S8'!$E$6:$E$23,"Ambos")+SUMIFS('S9'!$I$6:$I$15,'S9'!$B$6:$B$15,$A92,'S9'!$E$6:$E$15,"Víctor")+SUMIFS('S9'!$I$6:$I$15,'S9'!$B$6:$B$15,$A92,'S9'!$E$6:$E$15,"Ambos")+SUMIFS('S10'!$I$6:$I$13,'S10'!$B$6:$B$13,$A92,'S10'!$E$6:$E$13,"Víctor")+SUMIFS('S10'!$I$6:$I$13,'S10'!$B$6:$B$13,$A92,'S10'!$E$6:$E$13,"Ambos")+SUMIFS('Holgura'!$I$6:$I$11,'Holgura'!$B$6:$B$11,$A92,'Holgura'!$E$6:$E$11,"Víctor")+SUMIFS('Holgura'!$I$6:$I$11,'Holgura'!$B$6:$B$11,$A92,'Holgura'!$E$6:$E$11,"Ambos")+SUMIFS('Entrega'!$I$6:$I$9,'Entrega'!$B$6:$B$9,$A92,'Entrega'!$E$6:$E$9,"Víctor")+SUMIFS('Entrega'!$I$6:$I$9,'Entrega'!$B$6:$B$9,$A92,'Entrega'!$E$6:$E$9,"Ambos")+SUMIFS('Defensa'!$I$6:$I$10,'Defensa'!$B$6:$B$10,$A92,'Defensa'!$E$6:$E$10,"Víctor")+SUMIFS('Defensa'!$I$6:$I$10,'Defensa'!$B$6:$B$10,$A92,'Defensa'!$E$6:$E$10,"Ambos")</f>
         <v/>
       </c>
       <c r="E92" s="21">
-        <f>SUMIFS('S1'!$I$6:$I$32,'S1'!$B$6:$B$32,$A92,'S1'!$E$6:$E$32,"Diego")+SUMIFS('S1'!$I$6:$I$32,'S1'!$B$6:$B$32,$A92,'S1'!$E$6:$E$32,"Ambos")+SUMIFS('S2'!$I$6:$I$23,'S2'!$B$6:$B$23,$A92,'S2'!$E$6:$E$23,"Diego")+SUMIFS('S2'!$I$6:$I$23,'S2'!$B$6:$B$23,$A92,'S2'!$E$6:$E$23,"Ambos")+SUMIFS('S3'!$I$6:$I$19,'S3'!$B$6:$B$19,$A92,'S3'!$E$6:$E$19,"Diego")+SUMIFS('S3'!$I$6:$I$19,'S3'!$B$6:$B$19,$A92,'S3'!$E$6:$E$19,"Ambos")+SUMIFS('S4'!$I$6:$I$20,'S4'!$B$6:$B$20,$A92,'S4'!$E$6:$E$20,"Diego")+SUMIFS('S4'!$I$6:$I$20,'S4'!$B$6:$B$20,$A92,'S4'!$E$6:$E$20,"Ambos")+SUMIFS('S5'!$I$6:$I$20,'S5'!$B$6:$B$20,$A92,'S5'!$E$6:$E$20,"Diego")+SUMIFS('S5'!$I$6:$I$20,'S5'!$B$6:$B$20,$A92,'S5'!$E$6:$E$20,"Ambos")+SUMIFS('S6'!$I$6:$I$17,'S6'!$B$6:$B$17,$A92,'S6'!$E$6:$E$17,"Diego")+SUMIFS('S6'!$I$6:$I$17,'S6'!$B$6:$B$17,$A92,'S6'!$E$6:$E$17,"Ambos")+SUMIFS('S7'!$I$6:$I$19,'S7'!$B$6:$B$19,$A92,'S7'!$E$6:$E$19,"Diego")+SUMIFS('S7'!$I$6:$I$19,'S7'!$B$6:$B$19,$A92,'S7'!$E$6:$E$19,"Ambos")+SUMIFS('S8'!$I$6:$I$23,'S8'!$B$6:$B$23,$A92,'S8'!$E$6:$E$23,"Diego")+SUMIFS('S8'!$I$6:$I$23,'S8'!$B$6:$B$23,$A92,'S8'!$E$6:$E$23,"Ambos")+SUMIFS('S9'!$I$6:$I$15,'S9'!$B$6:$B$15,$A92,'S9'!$E$6:$E$15,"Diego")+SUMIFS('S9'!$I$6:$I$15,'S9'!$B$6:$B$15,$A92,'S9'!$E$6:$E$15,"Ambos")+SUMIFS('S10'!$I$6:$I$13,'S10'!$B$6:$B$13,$A92,'S10'!$E$6:$E$13,"Diego")+SUMIFS('S10'!$I$6:$I$13,'S10'!$B$6:$B$13,$A92,'S10'!$E$6:$E$13,"Ambos")+SUMIFS('Holgura'!$I$6:$I$11,'Holgura'!$B$6:$B$11,$A92,'Holgura'!$E$6:$E$11,"Diego")+SUMIFS('Holgura'!$I$6:$I$11,'Holgura'!$B$6:$B$11,$A92,'Holgura'!$E$6:$E$11,"Ambos")+SUMIFS('Entrega'!$I$6:$I$9,'Entrega'!$B$6:$B$9,$A92,'Entrega'!$E$6:$E$9,"Diego")+SUMIFS('Entrega'!$I$6:$I$9,'Entrega'!$B$6:$B$9,$A92,'Entrega'!$E$6:$E$9,"Ambos")+SUMIFS('Defensa'!$I$6:$I$10,'Defensa'!$B$6:$B$10,$A92,'Defensa'!$E$6:$E$10,"Diego")+SUMIFS('Defensa'!$I$6:$I$10,'Defensa'!$B$6:$B$10,$A92,'Defensa'!$E$6:$E$10,"Ambos")</f>
+        <f>SUMIFS('S1'!$I$6:$I$32,'S1'!$B$6:$B$32,$A92,'S1'!$E$6:$E$32,"Diego")+SUMIFS('S1'!$I$6:$I$32,'S1'!$B$6:$B$32,$A92,'S1'!$E$6:$E$32,"Ambos")+SUMIFS('S2'!$I$6:$I$23,'S2'!$B$6:$B$23,$A92,'S2'!$E$6:$E$23,"Diego")+SUMIFS('S2'!$I$6:$I$23,'S2'!$B$6:$B$23,$A92,'S2'!$E$6:$E$23,"Ambos")+SUMIFS('S3'!$I$6:$I$24,'S3'!$B$6:$B$24,$A92,'S3'!$E$6:$E$24,"Diego")+SUMIFS('S3'!$I$6:$I$24,'S3'!$B$6:$B$24,$A92,'S3'!$E$6:$E$24,"Ambos")+SUMIFS('S4'!$I$6:$I$22,'S4'!$B$6:$B$22,$A92,'S4'!$E$6:$E$22,"Diego")+SUMIFS('S4'!$I$6:$I$22,'S4'!$B$6:$B$22,$A92,'S4'!$E$6:$E$22,"Ambos")+SUMIFS('S5'!$I$6:$I$20,'S5'!$B$6:$B$20,$A92,'S5'!$E$6:$E$20,"Diego")+SUMIFS('S5'!$I$6:$I$20,'S5'!$B$6:$B$20,$A92,'S5'!$E$6:$E$20,"Ambos")+SUMIFS('S6'!$I$6:$I$17,'S6'!$B$6:$B$17,$A92,'S6'!$E$6:$E$17,"Diego")+SUMIFS('S6'!$I$6:$I$17,'S6'!$B$6:$B$17,$A92,'S6'!$E$6:$E$17,"Ambos")+SUMIFS('S7'!$I$6:$I$19,'S7'!$B$6:$B$19,$A92,'S7'!$E$6:$E$19,"Diego")+SUMIFS('S7'!$I$6:$I$19,'S7'!$B$6:$B$19,$A92,'S7'!$E$6:$E$19,"Ambos")+SUMIFS('S8'!$I$6:$I$23,'S8'!$B$6:$B$23,$A92,'S8'!$E$6:$E$23,"Diego")+SUMIFS('S8'!$I$6:$I$23,'S8'!$B$6:$B$23,$A92,'S8'!$E$6:$E$23,"Ambos")+SUMIFS('S9'!$I$6:$I$15,'S9'!$B$6:$B$15,$A92,'S9'!$E$6:$E$15,"Diego")+SUMIFS('S9'!$I$6:$I$15,'S9'!$B$6:$B$15,$A92,'S9'!$E$6:$E$15,"Ambos")+SUMIFS('S10'!$I$6:$I$13,'S10'!$B$6:$B$13,$A92,'S10'!$E$6:$E$13,"Diego")+SUMIFS('S10'!$I$6:$I$13,'S10'!$B$6:$B$13,$A92,'S10'!$E$6:$E$13,"Ambos")+SUMIFS('Holgura'!$I$6:$I$11,'Holgura'!$B$6:$B$11,$A92,'Holgura'!$E$6:$E$11,"Diego")+SUMIFS('Holgura'!$I$6:$I$11,'Holgura'!$B$6:$B$11,$A92,'Holgura'!$E$6:$E$11,"Ambos")+SUMIFS('Entrega'!$I$6:$I$9,'Entrega'!$B$6:$B$9,$A92,'Entrega'!$E$6:$E$9,"Diego")+SUMIFS('Entrega'!$I$6:$I$9,'Entrega'!$B$6:$B$9,$A92,'Entrega'!$E$6:$E$9,"Ambos")+SUMIFS('Defensa'!$I$6:$I$10,'Defensa'!$B$6:$B$10,$A92,'Defensa'!$E$6:$E$10,"Diego")+SUMIFS('Defensa'!$I$6:$I$10,'Defensa'!$B$6:$B$10,$A92,'Defensa'!$E$6:$E$10,"Ambos")</f>
         <v/>
       </c>
       <c r="F92" s="21">
-        <f>COUNTIFS('S1'!$B$6:$B$32,$A92,'S1'!$E$6:$E$32,"Víctor")+COUNTIFS('S1'!$B$6:$B$32,$A92,'S1'!$E$6:$E$32,"Ambos")+COUNTIFS('S2'!$B$6:$B$23,$A92,'S2'!$E$6:$E$23,"Víctor")+COUNTIFS('S2'!$B$6:$B$23,$A92,'S2'!$E$6:$E$23,"Ambos")+COUNTIFS('S3'!$B$6:$B$19,$A92,'S3'!$E$6:$E$19,"Víctor")+COUNTIFS('S3'!$B$6:$B$19,$A92,'S3'!$E$6:$E$19,"Ambos")+COUNTIFS('S4'!$B$6:$B$20,$A92,'S4'!$E$6:$E$20,"Víctor")+COUNTIFS('S4'!$B$6:$B$20,$A92,'S4'!$E$6:$E$20,"Ambos")+COUNTIFS('S5'!$B$6:$B$20,$A92,'S5'!$E$6:$E$20,"Víctor")+COUNTIFS('S5'!$B$6:$B$20,$A92,'S5'!$E$6:$E$20,"Ambos")+COUNTIFS('S6'!$B$6:$B$17,$A92,'S6'!$E$6:$E$17,"Víctor")+COUNTIFS('S6'!$B$6:$B$17,$A92,'S6'!$E$6:$E$17,"Ambos")+COUNTIFS('S7'!$B$6:$B$19,$A92,'S7'!$E$6:$E$19,"Víctor")+COUNTIFS('S7'!$B$6:$B$19,$A92,'S7'!$E$6:$E$19,"Ambos")+COUNTIFS('S8'!$B$6:$B$23,$A92,'S8'!$E$6:$E$23,"Víctor")+COUNTIFS('S8'!$B$6:$B$23,$A92,'S8'!$E$6:$E$23,"Ambos")+COUNTIFS('S9'!$B$6:$B$15,$A92,'S9'!$E$6:$E$15,"Víctor")+COUNTIFS('S9'!$B$6:$B$15,$A92,'S9'!$E$6:$E$15,"Ambos")+COUNTIFS('S10'!$B$6:$B$13,$A92,'S10'!$E$6:$E$13,"Víctor")+COUNTIFS('S10'!$B$6:$B$13,$A92,'S10'!$E$6:$E$13,"Ambos")+COUNTIFS('Holgura'!$B$6:$B$11,$A92,'Holgura'!$E$6:$E$11,"Víctor")+COUNTIFS('Holgura'!$B$6:$B$11,$A92,'Holgura'!$E$6:$E$11,"Ambos")+COUNTIFS('Entrega'!$B$6:$B$9,$A92,'Entrega'!$E$6:$E$9,"Víctor")+COUNTIFS('Entrega'!$B$6:$B$9,$A92,'Entrega'!$E$6:$E$9,"Ambos")+COUNTIFS('Defensa'!$B$6:$B$10,$A92,'Defensa'!$E$6:$E$10,"Víctor")+COUNTIFS('Defensa'!$B$6:$B$10,$A92,'Defensa'!$E$6:$E$10,"Ambos")</f>
+        <f>COUNTIFS('S1'!$B$6:$B$32,$A92,'S1'!$E$6:$E$32,"Víctor")+COUNTIFS('S1'!$B$6:$B$32,$A92,'S1'!$E$6:$E$32,"Ambos")+COUNTIFS('S2'!$B$6:$B$23,$A92,'S2'!$E$6:$E$23,"Víctor")+COUNTIFS('S2'!$B$6:$B$23,$A92,'S2'!$E$6:$E$23,"Ambos")+COUNTIFS('S3'!$B$6:$B$24,$A92,'S3'!$E$6:$E$24,"Víctor")+COUNTIFS('S3'!$B$6:$B$24,$A92,'S3'!$E$6:$E$24,"Ambos")+COUNTIFS('S4'!$B$6:$B$22,$A92,'S4'!$E$6:$E$22,"Víctor")+COUNTIFS('S4'!$B$6:$B$22,$A92,'S4'!$E$6:$E$22,"Ambos")+COUNTIFS('S5'!$B$6:$B$20,$A92,'S5'!$E$6:$E$20,"Víctor")+COUNTIFS('S5'!$B$6:$B$20,$A92,'S5'!$E$6:$E$20,"Ambos")+COUNTIFS('S6'!$B$6:$B$17,$A92,'S6'!$E$6:$E$17,"Víctor")+COUNTIFS('S6'!$B$6:$B$17,$A92,'S6'!$E$6:$E$17,"Ambos")+COUNTIFS('S7'!$B$6:$B$19,$A92,'S7'!$E$6:$E$19,"Víctor")+COUNTIFS('S7'!$B$6:$B$19,$A92,'S7'!$E$6:$E$19,"Ambos")+COUNTIFS('S8'!$B$6:$B$23,$A92,'S8'!$E$6:$E$23,"Víctor")+COUNTIFS('S8'!$B$6:$B$23,$A92,'S8'!$E$6:$E$23,"Ambos")+COUNTIFS('S9'!$B$6:$B$15,$A92,'S9'!$E$6:$E$15,"Víctor")+COUNTIFS('S9'!$B$6:$B$15,$A92,'S9'!$E$6:$E$15,"Ambos")+COUNTIFS('S10'!$B$6:$B$13,$A92,'S10'!$E$6:$E$13,"Víctor")+COUNTIFS('S10'!$B$6:$B$13,$A92,'S10'!$E$6:$E$13,"Ambos")+COUNTIFS('Holgura'!$B$6:$B$11,$A92,'Holgura'!$E$6:$E$11,"Víctor")+COUNTIFS('Holgura'!$B$6:$B$11,$A92,'Holgura'!$E$6:$E$11,"Ambos")+COUNTIFS('Entrega'!$B$6:$B$9,$A92,'Entrega'!$E$6:$E$9,"Víctor")+COUNTIFS('Entrega'!$B$6:$B$9,$A92,'Entrega'!$E$6:$E$9,"Ambos")+COUNTIFS('Defensa'!$B$6:$B$10,$A92,'Defensa'!$E$6:$E$10,"Víctor")+COUNTIFS('Defensa'!$B$6:$B$10,$A92,'Defensa'!$E$6:$E$10,"Ambos")</f>
         <v/>
       </c>
       <c r="G92" s="21">
-        <f>COUNTIFS('S1'!$B$6:$B$32,$A92,'S1'!$E$6:$E$32,"Diego")+COUNTIFS('S1'!$B$6:$B$32,$A92,'S1'!$E$6:$E$32,"Ambos")+COUNTIFS('S2'!$B$6:$B$23,$A92,'S2'!$E$6:$E$23,"Diego")+COUNTIFS('S2'!$B$6:$B$23,$A92,'S2'!$E$6:$E$23,"Ambos")+COUNTIFS('S3'!$B$6:$B$19,$A92,'S3'!$E$6:$E$19,"Diego")+COUNTIFS('S3'!$B$6:$B$19,$A92,'S3'!$E$6:$E$19,"Ambos")+COUNTIFS('S4'!$B$6:$B$20,$A92,'S4'!$E$6:$E$20,"Diego")+COUNTIFS('S4'!$B$6:$B$20,$A92,'S4'!$E$6:$E$20,"Ambos")+COUNTIFS('S5'!$B$6:$B$20,$A92,'S5'!$E$6:$E$20,"Diego")+COUNTIFS('S5'!$B$6:$B$20,$A92,'S5'!$E$6:$E$20,"Ambos")+COUNTIFS('S6'!$B$6:$B$17,$A92,'S6'!$E$6:$E$17,"Diego")+COUNTIFS('S6'!$B$6:$B$17,$A92,'S6'!$E$6:$E$17,"Ambos")+COUNTIFS('S7'!$B$6:$B$19,$A92,'S7'!$E$6:$E$19,"Diego")+COUNTIFS('S7'!$B$6:$B$19,$A92,'S7'!$E$6:$E$19,"Ambos")+COUNTIFS('S8'!$B$6:$B$23,$A92,'S8'!$E$6:$E$23,"Diego")+COUNTIFS('S8'!$B$6:$B$23,$A92,'S8'!$E$6:$E$23,"Ambos")+COUNTIFS('S9'!$B$6:$B$15,$A92,'S9'!$E$6:$E$15,"Diego")+COUNTIFS('S9'!$B$6:$B$15,$A92,'S9'!$E$6:$E$15,"Ambos")+COUNTIFS('S10'!$B$6:$B$13,$A92,'S10'!$E$6:$E$13,"Diego")+COUNTIFS('S10'!$B$6:$B$13,$A92,'S10'!$E$6:$E$13,"Ambos")+COUNTIFS('Holgura'!$B$6:$B$11,$A92,'Holgura'!$E$6:$E$11,"Diego")+COUNTIFS('Holgura'!$B$6:$B$11,$A92,'Holgura'!$E$6:$E$11,"Ambos")+COUNTIFS('Entrega'!$B$6:$B$9,$A92,'Entrega'!$E$6:$E$9,"Diego")+COUNTIFS('Entrega'!$B$6:$B$9,$A92,'Entrega'!$E$6:$E$9,"Ambos")+COUNTIFS('Defensa'!$B$6:$B$10,$A92,'Defensa'!$E$6:$E$10,"Diego")+COUNTIFS('Defensa'!$B$6:$B$10,$A92,'Defensa'!$E$6:$E$10,"Ambos")</f>
+        <f>COUNTIFS('S1'!$B$6:$B$32,$A92,'S1'!$E$6:$E$32,"Diego")+COUNTIFS('S1'!$B$6:$B$32,$A92,'S1'!$E$6:$E$32,"Ambos")+COUNTIFS('S2'!$B$6:$B$23,$A92,'S2'!$E$6:$E$23,"Diego")+COUNTIFS('S2'!$B$6:$B$23,$A92,'S2'!$E$6:$E$23,"Ambos")+COUNTIFS('S3'!$B$6:$B$24,$A92,'S3'!$E$6:$E$24,"Diego")+COUNTIFS('S3'!$B$6:$B$24,$A92,'S3'!$E$6:$E$24,"Ambos")+COUNTIFS('S4'!$B$6:$B$22,$A92,'S4'!$E$6:$E$22,"Diego")+COUNTIFS('S4'!$B$6:$B$22,$A92,'S4'!$E$6:$E$22,"Ambos")+COUNTIFS('S5'!$B$6:$B$20,$A92,'S5'!$E$6:$E$20,"Diego")+COUNTIFS('S5'!$B$6:$B$20,$A92,'S5'!$E$6:$E$20,"Ambos")+COUNTIFS('S6'!$B$6:$B$17,$A92,'S6'!$E$6:$E$17,"Diego")+COUNTIFS('S6'!$B$6:$B$17,$A92,'S6'!$E$6:$E$17,"Ambos")+COUNTIFS('S7'!$B$6:$B$19,$A92,'S7'!$E$6:$E$19,"Diego")+COUNTIFS('S7'!$B$6:$B$19,$A92,'S7'!$E$6:$E$19,"Ambos")+COUNTIFS('S8'!$B$6:$B$23,$A92,'S8'!$E$6:$E$23,"Diego")+COUNTIFS('S8'!$B$6:$B$23,$A92,'S8'!$E$6:$E$23,"Ambos")+COUNTIFS('S9'!$B$6:$B$15,$A92,'S9'!$E$6:$E$15,"Diego")+COUNTIFS('S9'!$B$6:$B$15,$A92,'S9'!$E$6:$E$15,"Ambos")+COUNTIFS('S10'!$B$6:$B$13,$A92,'S10'!$E$6:$E$13,"Diego")+COUNTIFS('S10'!$B$6:$B$13,$A92,'S10'!$E$6:$E$13,"Ambos")+COUNTIFS('Holgura'!$B$6:$B$11,$A92,'Holgura'!$E$6:$E$11,"Diego")+COUNTIFS('Holgura'!$B$6:$B$11,$A92,'Holgura'!$E$6:$E$11,"Ambos")+COUNTIFS('Entrega'!$B$6:$B$9,$A92,'Entrega'!$E$6:$E$9,"Diego")+COUNTIFS('Entrega'!$B$6:$B$9,$A92,'Entrega'!$E$6:$E$9,"Ambos")+COUNTIFS('Defensa'!$B$6:$B$10,$A92,'Defensa'!$E$6:$E$10,"Diego")+COUNTIFS('Defensa'!$B$6:$B$10,$A92,'Defensa'!$E$6:$E$10,"Ambos")</f>
         <v/>
       </c>
     </row>
@@ -11232,19 +11253,19 @@
         <v/>
       </c>
       <c r="D93" s="21">
-        <f>SUMIFS('S1'!$I$6:$I$32,'S1'!$B$6:$B$32,$A93,'S1'!$E$6:$E$32,"Víctor")+SUMIFS('S1'!$I$6:$I$32,'S1'!$B$6:$B$32,$A93,'S1'!$E$6:$E$32,"Ambos")+SUMIFS('S2'!$I$6:$I$23,'S2'!$B$6:$B$23,$A93,'S2'!$E$6:$E$23,"Víctor")+SUMIFS('S2'!$I$6:$I$23,'S2'!$B$6:$B$23,$A93,'S2'!$E$6:$E$23,"Ambos")+SUMIFS('S3'!$I$6:$I$19,'S3'!$B$6:$B$19,$A93,'S3'!$E$6:$E$19,"Víctor")+SUMIFS('S3'!$I$6:$I$19,'S3'!$B$6:$B$19,$A93,'S3'!$E$6:$E$19,"Ambos")+SUMIFS('S4'!$I$6:$I$20,'S4'!$B$6:$B$20,$A93,'S4'!$E$6:$E$20,"Víctor")+SUMIFS('S4'!$I$6:$I$20,'S4'!$B$6:$B$20,$A93,'S4'!$E$6:$E$20,"Ambos")+SUMIFS('S5'!$I$6:$I$20,'S5'!$B$6:$B$20,$A93,'S5'!$E$6:$E$20,"Víctor")+SUMIFS('S5'!$I$6:$I$20,'S5'!$B$6:$B$20,$A93,'S5'!$E$6:$E$20,"Ambos")+SUMIFS('S6'!$I$6:$I$17,'S6'!$B$6:$B$17,$A93,'S6'!$E$6:$E$17,"Víctor")+SUMIFS('S6'!$I$6:$I$17,'S6'!$B$6:$B$17,$A93,'S6'!$E$6:$E$17,"Ambos")+SUMIFS('S7'!$I$6:$I$19,'S7'!$B$6:$B$19,$A93,'S7'!$E$6:$E$19,"Víctor")+SUMIFS('S7'!$I$6:$I$19,'S7'!$B$6:$B$19,$A93,'S7'!$E$6:$E$19,"Ambos")+SUMIFS('S8'!$I$6:$I$23,'S8'!$B$6:$B$23,$A93,'S8'!$E$6:$E$23,"Víctor")+SUMIFS('S8'!$I$6:$I$23,'S8'!$B$6:$B$23,$A93,'S8'!$E$6:$E$23,"Ambos")+SUMIFS('S9'!$I$6:$I$15,'S9'!$B$6:$B$15,$A93,'S9'!$E$6:$E$15,"Víctor")+SUMIFS('S9'!$I$6:$I$15,'S9'!$B$6:$B$15,$A93,'S9'!$E$6:$E$15,"Ambos")+SUMIFS('S10'!$I$6:$I$13,'S10'!$B$6:$B$13,$A93,'S10'!$E$6:$E$13,"Víctor")+SUMIFS('S10'!$I$6:$I$13,'S10'!$B$6:$B$13,$A93,'S10'!$E$6:$E$13,"Ambos")+SUMIFS('Holgura'!$I$6:$I$11,'Holgura'!$B$6:$B$11,$A93,'Holgura'!$E$6:$E$11,"Víctor")+SUMIFS('Holgura'!$I$6:$I$11,'Holgura'!$B$6:$B$11,$A93,'Holgura'!$E$6:$E$11,"Ambos")+SUMIFS('Entrega'!$I$6:$I$9,'Entrega'!$B$6:$B$9,$A93,'Entrega'!$E$6:$E$9,"Víctor")+SUMIFS('Entrega'!$I$6:$I$9,'Entrega'!$B$6:$B$9,$A93,'Entrega'!$E$6:$E$9,"Ambos")+SUMIFS('Defensa'!$I$6:$I$10,'Defensa'!$B$6:$B$10,$A93,'Defensa'!$E$6:$E$10,"Víctor")+SUMIFS('Defensa'!$I$6:$I$10,'Defensa'!$B$6:$B$10,$A93,'Defensa'!$E$6:$E$10,"Ambos")</f>
+        <f>SUMIFS('S1'!$I$6:$I$32,'S1'!$B$6:$B$32,$A93,'S1'!$E$6:$E$32,"Víctor")+SUMIFS('S1'!$I$6:$I$32,'S1'!$B$6:$B$32,$A93,'S1'!$E$6:$E$32,"Ambos")+SUMIFS('S2'!$I$6:$I$23,'S2'!$B$6:$B$23,$A93,'S2'!$E$6:$E$23,"Víctor")+SUMIFS('S2'!$I$6:$I$23,'S2'!$B$6:$B$23,$A93,'S2'!$E$6:$E$23,"Ambos")+SUMIFS('S3'!$I$6:$I$24,'S3'!$B$6:$B$24,$A93,'S3'!$E$6:$E$24,"Víctor")+SUMIFS('S3'!$I$6:$I$24,'S3'!$B$6:$B$24,$A93,'S3'!$E$6:$E$24,"Ambos")+SUMIFS('S4'!$I$6:$I$22,'S4'!$B$6:$B$22,$A93,'S4'!$E$6:$E$22,"Víctor")+SUMIFS('S4'!$I$6:$I$22,'S4'!$B$6:$B$22,$A93,'S4'!$E$6:$E$22,"Ambos")+SUMIFS('S5'!$I$6:$I$20,'S5'!$B$6:$B$20,$A93,'S5'!$E$6:$E$20,"Víctor")+SUMIFS('S5'!$I$6:$I$20,'S5'!$B$6:$B$20,$A93,'S5'!$E$6:$E$20,"Ambos")+SUMIFS('S6'!$I$6:$I$17,'S6'!$B$6:$B$17,$A93,'S6'!$E$6:$E$17,"Víctor")+SUMIFS('S6'!$I$6:$I$17,'S6'!$B$6:$B$17,$A93,'S6'!$E$6:$E$17,"Ambos")+SUMIFS('S7'!$I$6:$I$19,'S7'!$B$6:$B$19,$A93,'S7'!$E$6:$E$19,"Víctor")+SUMIFS('S7'!$I$6:$I$19,'S7'!$B$6:$B$19,$A93,'S7'!$E$6:$E$19,"Ambos")+SUMIFS('S8'!$I$6:$I$23,'S8'!$B$6:$B$23,$A93,'S8'!$E$6:$E$23,"Víctor")+SUMIFS('S8'!$I$6:$I$23,'S8'!$B$6:$B$23,$A93,'S8'!$E$6:$E$23,"Ambos")+SUMIFS('S9'!$I$6:$I$15,'S9'!$B$6:$B$15,$A93,'S9'!$E$6:$E$15,"Víctor")+SUMIFS('S9'!$I$6:$I$15,'S9'!$B$6:$B$15,$A93,'S9'!$E$6:$E$15,"Ambos")+SUMIFS('S10'!$I$6:$I$13,'S10'!$B$6:$B$13,$A93,'S10'!$E$6:$E$13,"Víctor")+SUMIFS('S10'!$I$6:$I$13,'S10'!$B$6:$B$13,$A93,'S10'!$E$6:$E$13,"Ambos")+SUMIFS('Holgura'!$I$6:$I$11,'Holgura'!$B$6:$B$11,$A93,'Holgura'!$E$6:$E$11,"Víctor")+SUMIFS('Holgura'!$I$6:$I$11,'Holgura'!$B$6:$B$11,$A93,'Holgura'!$E$6:$E$11,"Ambos")+SUMIFS('Entrega'!$I$6:$I$9,'Entrega'!$B$6:$B$9,$A93,'Entrega'!$E$6:$E$9,"Víctor")+SUMIFS('Entrega'!$I$6:$I$9,'Entrega'!$B$6:$B$9,$A93,'Entrega'!$E$6:$E$9,"Ambos")+SUMIFS('Defensa'!$I$6:$I$10,'Defensa'!$B$6:$B$10,$A93,'Defensa'!$E$6:$E$10,"Víctor")+SUMIFS('Defensa'!$I$6:$I$10,'Defensa'!$B$6:$B$10,$A93,'Defensa'!$E$6:$E$10,"Ambos")</f>
         <v/>
       </c>
       <c r="E93" s="21">
-        <f>SUMIFS('S1'!$I$6:$I$32,'S1'!$B$6:$B$32,$A93,'S1'!$E$6:$E$32,"Diego")+SUMIFS('S1'!$I$6:$I$32,'S1'!$B$6:$B$32,$A93,'S1'!$E$6:$E$32,"Ambos")+SUMIFS('S2'!$I$6:$I$23,'S2'!$B$6:$B$23,$A93,'S2'!$E$6:$E$23,"Diego")+SUMIFS('S2'!$I$6:$I$23,'S2'!$B$6:$B$23,$A93,'S2'!$E$6:$E$23,"Ambos")+SUMIFS('S3'!$I$6:$I$19,'S3'!$B$6:$B$19,$A93,'S3'!$E$6:$E$19,"Diego")+SUMIFS('S3'!$I$6:$I$19,'S3'!$B$6:$B$19,$A93,'S3'!$E$6:$E$19,"Ambos")+SUMIFS('S4'!$I$6:$I$20,'S4'!$B$6:$B$20,$A93,'S4'!$E$6:$E$20,"Diego")+SUMIFS('S4'!$I$6:$I$20,'S4'!$B$6:$B$20,$A93,'S4'!$E$6:$E$20,"Ambos")+SUMIFS('S5'!$I$6:$I$20,'S5'!$B$6:$B$20,$A93,'S5'!$E$6:$E$20,"Diego")+SUMIFS('S5'!$I$6:$I$20,'S5'!$B$6:$B$20,$A93,'S5'!$E$6:$E$20,"Ambos")+SUMIFS('S6'!$I$6:$I$17,'S6'!$B$6:$B$17,$A93,'S6'!$E$6:$E$17,"Diego")+SUMIFS('S6'!$I$6:$I$17,'S6'!$B$6:$B$17,$A93,'S6'!$E$6:$E$17,"Ambos")+SUMIFS('S7'!$I$6:$I$19,'S7'!$B$6:$B$19,$A93,'S7'!$E$6:$E$19,"Diego")+SUMIFS('S7'!$I$6:$I$19,'S7'!$B$6:$B$19,$A93,'S7'!$E$6:$E$19,"Ambos")+SUMIFS('S8'!$I$6:$I$23,'S8'!$B$6:$B$23,$A93,'S8'!$E$6:$E$23,"Diego")+SUMIFS('S8'!$I$6:$I$23,'S8'!$B$6:$B$23,$A93,'S8'!$E$6:$E$23,"Ambos")+SUMIFS('S9'!$I$6:$I$15,'S9'!$B$6:$B$15,$A93,'S9'!$E$6:$E$15,"Diego")+SUMIFS('S9'!$I$6:$I$15,'S9'!$B$6:$B$15,$A93,'S9'!$E$6:$E$15,"Ambos")+SUMIFS('S10'!$I$6:$I$13,'S10'!$B$6:$B$13,$A93,'S10'!$E$6:$E$13,"Diego")+SUMIFS('S10'!$I$6:$I$13,'S10'!$B$6:$B$13,$A93,'S10'!$E$6:$E$13,"Ambos")+SUMIFS('Holgura'!$I$6:$I$11,'Holgura'!$B$6:$B$11,$A93,'Holgura'!$E$6:$E$11,"Diego")+SUMIFS('Holgura'!$I$6:$I$11,'Holgura'!$B$6:$B$11,$A93,'Holgura'!$E$6:$E$11,"Ambos")+SUMIFS('Entrega'!$I$6:$I$9,'Entrega'!$B$6:$B$9,$A93,'Entrega'!$E$6:$E$9,"Diego")+SUMIFS('Entrega'!$I$6:$I$9,'Entrega'!$B$6:$B$9,$A93,'Entrega'!$E$6:$E$9,"Ambos")+SUMIFS('Defensa'!$I$6:$I$10,'Defensa'!$B$6:$B$10,$A93,'Defensa'!$E$6:$E$10,"Diego")+SUMIFS('Defensa'!$I$6:$I$10,'Defensa'!$B$6:$B$10,$A93,'Defensa'!$E$6:$E$10,"Ambos")</f>
+        <f>SUMIFS('S1'!$I$6:$I$32,'S1'!$B$6:$B$32,$A93,'S1'!$E$6:$E$32,"Diego")+SUMIFS('S1'!$I$6:$I$32,'S1'!$B$6:$B$32,$A93,'S1'!$E$6:$E$32,"Ambos")+SUMIFS('S2'!$I$6:$I$23,'S2'!$B$6:$B$23,$A93,'S2'!$E$6:$E$23,"Diego")+SUMIFS('S2'!$I$6:$I$23,'S2'!$B$6:$B$23,$A93,'S2'!$E$6:$E$23,"Ambos")+SUMIFS('S3'!$I$6:$I$24,'S3'!$B$6:$B$24,$A93,'S3'!$E$6:$E$24,"Diego")+SUMIFS('S3'!$I$6:$I$24,'S3'!$B$6:$B$24,$A93,'S3'!$E$6:$E$24,"Ambos")+SUMIFS('S4'!$I$6:$I$22,'S4'!$B$6:$B$22,$A93,'S4'!$E$6:$E$22,"Diego")+SUMIFS('S4'!$I$6:$I$22,'S4'!$B$6:$B$22,$A93,'S4'!$E$6:$E$22,"Ambos")+SUMIFS('S5'!$I$6:$I$20,'S5'!$B$6:$B$20,$A93,'S5'!$E$6:$E$20,"Diego")+SUMIFS('S5'!$I$6:$I$20,'S5'!$B$6:$B$20,$A93,'S5'!$E$6:$E$20,"Ambos")+SUMIFS('S6'!$I$6:$I$17,'S6'!$B$6:$B$17,$A93,'S6'!$E$6:$E$17,"Diego")+SUMIFS('S6'!$I$6:$I$17,'S6'!$B$6:$B$17,$A93,'S6'!$E$6:$E$17,"Ambos")+SUMIFS('S7'!$I$6:$I$19,'S7'!$B$6:$B$19,$A93,'S7'!$E$6:$E$19,"Diego")+SUMIFS('S7'!$I$6:$I$19,'S7'!$B$6:$B$19,$A93,'S7'!$E$6:$E$19,"Ambos")+SUMIFS('S8'!$I$6:$I$23,'S8'!$B$6:$B$23,$A93,'S8'!$E$6:$E$23,"Diego")+SUMIFS('S8'!$I$6:$I$23,'S8'!$B$6:$B$23,$A93,'S8'!$E$6:$E$23,"Ambos")+SUMIFS('S9'!$I$6:$I$15,'S9'!$B$6:$B$15,$A93,'S9'!$E$6:$E$15,"Diego")+SUMIFS('S9'!$I$6:$I$15,'S9'!$B$6:$B$15,$A93,'S9'!$E$6:$E$15,"Ambos")+SUMIFS('S10'!$I$6:$I$13,'S10'!$B$6:$B$13,$A93,'S10'!$E$6:$E$13,"Diego")+SUMIFS('S10'!$I$6:$I$13,'S10'!$B$6:$B$13,$A93,'S10'!$E$6:$E$13,"Ambos")+SUMIFS('Holgura'!$I$6:$I$11,'Holgura'!$B$6:$B$11,$A93,'Holgura'!$E$6:$E$11,"Diego")+SUMIFS('Holgura'!$I$6:$I$11,'Holgura'!$B$6:$B$11,$A93,'Holgura'!$E$6:$E$11,"Ambos")+SUMIFS('Entrega'!$I$6:$I$9,'Entrega'!$B$6:$B$9,$A93,'Entrega'!$E$6:$E$9,"Diego")+SUMIFS('Entrega'!$I$6:$I$9,'Entrega'!$B$6:$B$9,$A93,'Entrega'!$E$6:$E$9,"Ambos")+SUMIFS('Defensa'!$I$6:$I$10,'Defensa'!$B$6:$B$10,$A93,'Defensa'!$E$6:$E$10,"Diego")+SUMIFS('Defensa'!$I$6:$I$10,'Defensa'!$B$6:$B$10,$A93,'Defensa'!$E$6:$E$10,"Ambos")</f>
         <v/>
       </c>
       <c r="F93" s="21">
-        <f>COUNTIFS('S1'!$B$6:$B$32,$A93,'S1'!$E$6:$E$32,"Víctor")+COUNTIFS('S1'!$B$6:$B$32,$A93,'S1'!$E$6:$E$32,"Ambos")+COUNTIFS('S2'!$B$6:$B$23,$A93,'S2'!$E$6:$E$23,"Víctor")+COUNTIFS('S2'!$B$6:$B$23,$A93,'S2'!$E$6:$E$23,"Ambos")+COUNTIFS('S3'!$B$6:$B$19,$A93,'S3'!$E$6:$E$19,"Víctor")+COUNTIFS('S3'!$B$6:$B$19,$A93,'S3'!$E$6:$E$19,"Ambos")+COUNTIFS('S4'!$B$6:$B$20,$A93,'S4'!$E$6:$E$20,"Víctor")+COUNTIFS('S4'!$B$6:$B$20,$A93,'S4'!$E$6:$E$20,"Ambos")+COUNTIFS('S5'!$B$6:$B$20,$A93,'S5'!$E$6:$E$20,"Víctor")+COUNTIFS('S5'!$B$6:$B$20,$A93,'S5'!$E$6:$E$20,"Ambos")+COUNTIFS('S6'!$B$6:$B$17,$A93,'S6'!$E$6:$E$17,"Víctor")+COUNTIFS('S6'!$B$6:$B$17,$A93,'S6'!$E$6:$E$17,"Ambos")+COUNTIFS('S7'!$B$6:$B$19,$A93,'S7'!$E$6:$E$19,"Víctor")+COUNTIFS('S7'!$B$6:$B$19,$A93,'S7'!$E$6:$E$19,"Ambos")+COUNTIFS('S8'!$B$6:$B$23,$A93,'S8'!$E$6:$E$23,"Víctor")+COUNTIFS('S8'!$B$6:$B$23,$A93,'S8'!$E$6:$E$23,"Ambos")+COUNTIFS('S9'!$B$6:$B$15,$A93,'S9'!$E$6:$E$15,"Víctor")+COUNTIFS('S9'!$B$6:$B$15,$A93,'S9'!$E$6:$E$15,"Ambos")+COUNTIFS('S10'!$B$6:$B$13,$A93,'S10'!$E$6:$E$13,"Víctor")+COUNTIFS('S10'!$B$6:$B$13,$A93,'S10'!$E$6:$E$13,"Ambos")+COUNTIFS('Holgura'!$B$6:$B$11,$A93,'Holgura'!$E$6:$E$11,"Víctor")+COUNTIFS('Holgura'!$B$6:$B$11,$A93,'Holgura'!$E$6:$E$11,"Ambos")+COUNTIFS('Entrega'!$B$6:$B$9,$A93,'Entrega'!$E$6:$E$9,"Víctor")+COUNTIFS('Entrega'!$B$6:$B$9,$A93,'Entrega'!$E$6:$E$9,"Ambos")+COUNTIFS('Defensa'!$B$6:$B$10,$A93,'Defensa'!$E$6:$E$10,"Víctor")+COUNTIFS('Defensa'!$B$6:$B$10,$A93,'Defensa'!$E$6:$E$10,"Ambos")</f>
+        <f>COUNTIFS('S1'!$B$6:$B$32,$A93,'S1'!$E$6:$E$32,"Víctor")+COUNTIFS('S1'!$B$6:$B$32,$A93,'S1'!$E$6:$E$32,"Ambos")+COUNTIFS('S2'!$B$6:$B$23,$A93,'S2'!$E$6:$E$23,"Víctor")+COUNTIFS('S2'!$B$6:$B$23,$A93,'S2'!$E$6:$E$23,"Ambos")+COUNTIFS('S3'!$B$6:$B$24,$A93,'S3'!$E$6:$E$24,"Víctor")+COUNTIFS('S3'!$B$6:$B$24,$A93,'S3'!$E$6:$E$24,"Ambos")+COUNTIFS('S4'!$B$6:$B$22,$A93,'S4'!$E$6:$E$22,"Víctor")+COUNTIFS('S4'!$B$6:$B$22,$A93,'S4'!$E$6:$E$22,"Ambos")+COUNTIFS('S5'!$B$6:$B$20,$A93,'S5'!$E$6:$E$20,"Víctor")+COUNTIFS('S5'!$B$6:$B$20,$A93,'S5'!$E$6:$E$20,"Ambos")+COUNTIFS('S6'!$B$6:$B$17,$A93,'S6'!$E$6:$E$17,"Víctor")+COUNTIFS('S6'!$B$6:$B$17,$A93,'S6'!$E$6:$E$17,"Ambos")+COUNTIFS('S7'!$B$6:$B$19,$A93,'S7'!$E$6:$E$19,"Víctor")+COUNTIFS('S7'!$B$6:$B$19,$A93,'S7'!$E$6:$E$19,"Ambos")+COUNTIFS('S8'!$B$6:$B$23,$A93,'S8'!$E$6:$E$23,"Víctor")+COUNTIFS('S8'!$B$6:$B$23,$A93,'S8'!$E$6:$E$23,"Ambos")+COUNTIFS('S9'!$B$6:$B$15,$A93,'S9'!$E$6:$E$15,"Víctor")+COUNTIFS('S9'!$B$6:$B$15,$A93,'S9'!$E$6:$E$15,"Ambos")+COUNTIFS('S10'!$B$6:$B$13,$A93,'S10'!$E$6:$E$13,"Víctor")+COUNTIFS('S10'!$B$6:$B$13,$A93,'S10'!$E$6:$E$13,"Ambos")+COUNTIFS('Holgura'!$B$6:$B$11,$A93,'Holgura'!$E$6:$E$11,"Víctor")+COUNTIFS('Holgura'!$B$6:$B$11,$A93,'Holgura'!$E$6:$E$11,"Ambos")+COUNTIFS('Entrega'!$B$6:$B$9,$A93,'Entrega'!$E$6:$E$9,"Víctor")+COUNTIFS('Entrega'!$B$6:$B$9,$A93,'Entrega'!$E$6:$E$9,"Ambos")+COUNTIFS('Defensa'!$B$6:$B$10,$A93,'Defensa'!$E$6:$E$10,"Víctor")+COUNTIFS('Defensa'!$B$6:$B$10,$A93,'Defensa'!$E$6:$E$10,"Ambos")</f>
         <v/>
       </c>
       <c r="G93" s="21">
-        <f>COUNTIFS('S1'!$B$6:$B$32,$A93,'S1'!$E$6:$E$32,"Diego")+COUNTIFS('S1'!$B$6:$B$32,$A93,'S1'!$E$6:$E$32,"Ambos")+COUNTIFS('S2'!$B$6:$B$23,$A93,'S2'!$E$6:$E$23,"Diego")+COUNTIFS('S2'!$B$6:$B$23,$A93,'S2'!$E$6:$E$23,"Ambos")+COUNTIFS('S3'!$B$6:$B$19,$A93,'S3'!$E$6:$E$19,"Diego")+COUNTIFS('S3'!$B$6:$B$19,$A93,'S3'!$E$6:$E$19,"Ambos")+COUNTIFS('S4'!$B$6:$B$20,$A93,'S4'!$E$6:$E$20,"Diego")+COUNTIFS('S4'!$B$6:$B$20,$A93,'S4'!$E$6:$E$20,"Ambos")+COUNTIFS('S5'!$B$6:$B$20,$A93,'S5'!$E$6:$E$20,"Diego")+COUNTIFS('S5'!$B$6:$B$20,$A93,'S5'!$E$6:$E$20,"Ambos")+COUNTIFS('S6'!$B$6:$B$17,$A93,'S6'!$E$6:$E$17,"Diego")+COUNTIFS('S6'!$B$6:$B$17,$A93,'S6'!$E$6:$E$17,"Ambos")+COUNTIFS('S7'!$B$6:$B$19,$A93,'S7'!$E$6:$E$19,"Diego")+COUNTIFS('S7'!$B$6:$B$19,$A93,'S7'!$E$6:$E$19,"Ambos")+COUNTIFS('S8'!$B$6:$B$23,$A93,'S8'!$E$6:$E$23,"Diego")+COUNTIFS('S8'!$B$6:$B$23,$A93,'S8'!$E$6:$E$23,"Ambos")+COUNTIFS('S9'!$B$6:$B$15,$A93,'S9'!$E$6:$E$15,"Diego")+COUNTIFS('S9'!$B$6:$B$15,$A93,'S9'!$E$6:$E$15,"Ambos")+COUNTIFS('S10'!$B$6:$B$13,$A93,'S10'!$E$6:$E$13,"Diego")+COUNTIFS('S10'!$B$6:$B$13,$A93,'S10'!$E$6:$E$13,"Ambos")+COUNTIFS('Holgura'!$B$6:$B$11,$A93,'Holgura'!$E$6:$E$11,"Diego")+COUNTIFS('Holgura'!$B$6:$B$11,$A93,'Holgura'!$E$6:$E$11,"Ambos")+COUNTIFS('Entrega'!$B$6:$B$9,$A93,'Entrega'!$E$6:$E$9,"Diego")+COUNTIFS('Entrega'!$B$6:$B$9,$A93,'Entrega'!$E$6:$E$9,"Ambos")+COUNTIFS('Defensa'!$B$6:$B$10,$A93,'Defensa'!$E$6:$E$10,"Diego")+COUNTIFS('Defensa'!$B$6:$B$10,$A93,'Defensa'!$E$6:$E$10,"Ambos")</f>
+        <f>COUNTIFS('S1'!$B$6:$B$32,$A93,'S1'!$E$6:$E$32,"Diego")+COUNTIFS('S1'!$B$6:$B$32,$A93,'S1'!$E$6:$E$32,"Ambos")+COUNTIFS('S2'!$B$6:$B$23,$A93,'S2'!$E$6:$E$23,"Diego")+COUNTIFS('S2'!$B$6:$B$23,$A93,'S2'!$E$6:$E$23,"Ambos")+COUNTIFS('S3'!$B$6:$B$24,$A93,'S3'!$E$6:$E$24,"Diego")+COUNTIFS('S3'!$B$6:$B$24,$A93,'S3'!$E$6:$E$24,"Ambos")+COUNTIFS('S4'!$B$6:$B$22,$A93,'S4'!$E$6:$E$22,"Diego")+COUNTIFS('S4'!$B$6:$B$22,$A93,'S4'!$E$6:$E$22,"Ambos")+COUNTIFS('S5'!$B$6:$B$20,$A93,'S5'!$E$6:$E$20,"Diego")+COUNTIFS('S5'!$B$6:$B$20,$A93,'S5'!$E$6:$E$20,"Ambos")+COUNTIFS('S6'!$B$6:$B$17,$A93,'S6'!$E$6:$E$17,"Diego")+COUNTIFS('S6'!$B$6:$B$17,$A93,'S6'!$E$6:$E$17,"Ambos")+COUNTIFS('S7'!$B$6:$B$19,$A93,'S7'!$E$6:$E$19,"Diego")+COUNTIFS('S7'!$B$6:$B$19,$A93,'S7'!$E$6:$E$19,"Ambos")+COUNTIFS('S8'!$B$6:$B$23,$A93,'S8'!$E$6:$E$23,"Diego")+COUNTIFS('S8'!$B$6:$B$23,$A93,'S8'!$E$6:$E$23,"Ambos")+COUNTIFS('S9'!$B$6:$B$15,$A93,'S9'!$E$6:$E$15,"Diego")+COUNTIFS('S9'!$B$6:$B$15,$A93,'S9'!$E$6:$E$15,"Ambos")+COUNTIFS('S10'!$B$6:$B$13,$A93,'S10'!$E$6:$E$13,"Diego")+COUNTIFS('S10'!$B$6:$B$13,$A93,'S10'!$E$6:$E$13,"Ambos")+COUNTIFS('Holgura'!$B$6:$B$11,$A93,'Holgura'!$E$6:$E$11,"Diego")+COUNTIFS('Holgura'!$B$6:$B$11,$A93,'Holgura'!$E$6:$E$11,"Ambos")+COUNTIFS('Entrega'!$B$6:$B$9,$A93,'Entrega'!$E$6:$E$9,"Diego")+COUNTIFS('Entrega'!$B$6:$B$9,$A93,'Entrega'!$E$6:$E$9,"Ambos")+COUNTIFS('Defensa'!$B$6:$B$10,$A93,'Defensa'!$E$6:$E$10,"Diego")+COUNTIFS('Defensa'!$B$6:$B$10,$A93,'Defensa'!$E$6:$E$10,"Ambos")</f>
         <v/>
       </c>
     </row>
@@ -11261,19 +11282,19 @@
         <v/>
       </c>
       <c r="D94" s="21">
-        <f>SUMIFS('S1'!$I$6:$I$32,'S1'!$B$6:$B$32,$A94,'S1'!$E$6:$E$32,"Víctor")+SUMIFS('S1'!$I$6:$I$32,'S1'!$B$6:$B$32,$A94,'S1'!$E$6:$E$32,"Ambos")+SUMIFS('S2'!$I$6:$I$23,'S2'!$B$6:$B$23,$A94,'S2'!$E$6:$E$23,"Víctor")+SUMIFS('S2'!$I$6:$I$23,'S2'!$B$6:$B$23,$A94,'S2'!$E$6:$E$23,"Ambos")+SUMIFS('S3'!$I$6:$I$19,'S3'!$B$6:$B$19,$A94,'S3'!$E$6:$E$19,"Víctor")+SUMIFS('S3'!$I$6:$I$19,'S3'!$B$6:$B$19,$A94,'S3'!$E$6:$E$19,"Ambos")+SUMIFS('S4'!$I$6:$I$20,'S4'!$B$6:$B$20,$A94,'S4'!$E$6:$E$20,"Víctor")+SUMIFS('S4'!$I$6:$I$20,'S4'!$B$6:$B$20,$A94,'S4'!$E$6:$E$20,"Ambos")+SUMIFS('S5'!$I$6:$I$20,'S5'!$B$6:$B$20,$A94,'S5'!$E$6:$E$20,"Víctor")+SUMIFS('S5'!$I$6:$I$20,'S5'!$B$6:$B$20,$A94,'S5'!$E$6:$E$20,"Ambos")+SUMIFS('S6'!$I$6:$I$17,'S6'!$B$6:$B$17,$A94,'S6'!$E$6:$E$17,"Víctor")+SUMIFS('S6'!$I$6:$I$17,'S6'!$B$6:$B$17,$A94,'S6'!$E$6:$E$17,"Ambos")+SUMIFS('S7'!$I$6:$I$19,'S7'!$B$6:$B$19,$A94,'S7'!$E$6:$E$19,"Víctor")+SUMIFS('S7'!$I$6:$I$19,'S7'!$B$6:$B$19,$A94,'S7'!$E$6:$E$19,"Ambos")+SUMIFS('S8'!$I$6:$I$23,'S8'!$B$6:$B$23,$A94,'S8'!$E$6:$E$23,"Víctor")+SUMIFS('S8'!$I$6:$I$23,'S8'!$B$6:$B$23,$A94,'S8'!$E$6:$E$23,"Ambos")+SUMIFS('S9'!$I$6:$I$15,'S9'!$B$6:$B$15,$A94,'S9'!$E$6:$E$15,"Víctor")+SUMIFS('S9'!$I$6:$I$15,'S9'!$B$6:$B$15,$A94,'S9'!$E$6:$E$15,"Ambos")+SUMIFS('S10'!$I$6:$I$13,'S10'!$B$6:$B$13,$A94,'S10'!$E$6:$E$13,"Víctor")+SUMIFS('S10'!$I$6:$I$13,'S10'!$B$6:$B$13,$A94,'S10'!$E$6:$E$13,"Ambos")+SUMIFS('Holgura'!$I$6:$I$11,'Holgura'!$B$6:$B$11,$A94,'Holgura'!$E$6:$E$11,"Víctor")+SUMIFS('Holgura'!$I$6:$I$11,'Holgura'!$B$6:$B$11,$A94,'Holgura'!$E$6:$E$11,"Ambos")+SUMIFS('Entrega'!$I$6:$I$9,'Entrega'!$B$6:$B$9,$A94,'Entrega'!$E$6:$E$9,"Víctor")+SUMIFS('Entrega'!$I$6:$I$9,'Entrega'!$B$6:$B$9,$A94,'Entrega'!$E$6:$E$9,"Ambos")+SUMIFS('Defensa'!$I$6:$I$10,'Defensa'!$B$6:$B$10,$A94,'Defensa'!$E$6:$E$10,"Víctor")+SUMIFS('Defensa'!$I$6:$I$10,'Defensa'!$B$6:$B$10,$A94,'Defensa'!$E$6:$E$10,"Ambos")</f>
+        <f>SUMIFS('S1'!$I$6:$I$32,'S1'!$B$6:$B$32,$A94,'S1'!$E$6:$E$32,"Víctor")+SUMIFS('S1'!$I$6:$I$32,'S1'!$B$6:$B$32,$A94,'S1'!$E$6:$E$32,"Ambos")+SUMIFS('S2'!$I$6:$I$23,'S2'!$B$6:$B$23,$A94,'S2'!$E$6:$E$23,"Víctor")+SUMIFS('S2'!$I$6:$I$23,'S2'!$B$6:$B$23,$A94,'S2'!$E$6:$E$23,"Ambos")+SUMIFS('S3'!$I$6:$I$24,'S3'!$B$6:$B$24,$A94,'S3'!$E$6:$E$24,"Víctor")+SUMIFS('S3'!$I$6:$I$24,'S3'!$B$6:$B$24,$A94,'S3'!$E$6:$E$24,"Ambos")+SUMIFS('S4'!$I$6:$I$22,'S4'!$B$6:$B$22,$A94,'S4'!$E$6:$E$22,"Víctor")+SUMIFS('S4'!$I$6:$I$22,'S4'!$B$6:$B$22,$A94,'S4'!$E$6:$E$22,"Ambos")+SUMIFS('S5'!$I$6:$I$20,'S5'!$B$6:$B$20,$A94,'S5'!$E$6:$E$20,"Víctor")+SUMIFS('S5'!$I$6:$I$20,'S5'!$B$6:$B$20,$A94,'S5'!$E$6:$E$20,"Ambos")+SUMIFS('S6'!$I$6:$I$17,'S6'!$B$6:$B$17,$A94,'S6'!$E$6:$E$17,"Víctor")+SUMIFS('S6'!$I$6:$I$17,'S6'!$B$6:$B$17,$A94,'S6'!$E$6:$E$17,"Ambos")+SUMIFS('S7'!$I$6:$I$19,'S7'!$B$6:$B$19,$A94,'S7'!$E$6:$E$19,"Víctor")+SUMIFS('S7'!$I$6:$I$19,'S7'!$B$6:$B$19,$A94,'S7'!$E$6:$E$19,"Ambos")+SUMIFS('S8'!$I$6:$I$23,'S8'!$B$6:$B$23,$A94,'S8'!$E$6:$E$23,"Víctor")+SUMIFS('S8'!$I$6:$I$23,'S8'!$B$6:$B$23,$A94,'S8'!$E$6:$E$23,"Ambos")+SUMIFS('S9'!$I$6:$I$15,'S9'!$B$6:$B$15,$A94,'S9'!$E$6:$E$15,"Víctor")+SUMIFS('S9'!$I$6:$I$15,'S9'!$B$6:$B$15,$A94,'S9'!$E$6:$E$15,"Ambos")+SUMIFS('S10'!$I$6:$I$13,'S10'!$B$6:$B$13,$A94,'S10'!$E$6:$E$13,"Víctor")+SUMIFS('S10'!$I$6:$I$13,'S10'!$B$6:$B$13,$A94,'S10'!$E$6:$E$13,"Ambos")+SUMIFS('Holgura'!$I$6:$I$11,'Holgura'!$B$6:$B$11,$A94,'Holgura'!$E$6:$E$11,"Víctor")+SUMIFS('Holgura'!$I$6:$I$11,'Holgura'!$B$6:$B$11,$A94,'Holgura'!$E$6:$E$11,"Ambos")+SUMIFS('Entrega'!$I$6:$I$9,'Entrega'!$B$6:$B$9,$A94,'Entrega'!$E$6:$E$9,"Víctor")+SUMIFS('Entrega'!$I$6:$I$9,'Entrega'!$B$6:$B$9,$A94,'Entrega'!$E$6:$E$9,"Ambos")+SUMIFS('Defensa'!$I$6:$I$10,'Defensa'!$B$6:$B$10,$A94,'Defensa'!$E$6:$E$10,"Víctor")+SUMIFS('Defensa'!$I$6:$I$10,'Defensa'!$B$6:$B$10,$A94,'Defensa'!$E$6:$E$10,"Ambos")</f>
         <v/>
       </c>
       <c r="E94" s="21">
-        <f>SUMIFS('S1'!$I$6:$I$32,'S1'!$B$6:$B$32,$A94,'S1'!$E$6:$E$32,"Diego")+SUMIFS('S1'!$I$6:$I$32,'S1'!$B$6:$B$32,$A94,'S1'!$E$6:$E$32,"Ambos")+SUMIFS('S2'!$I$6:$I$23,'S2'!$B$6:$B$23,$A94,'S2'!$E$6:$E$23,"Diego")+SUMIFS('S2'!$I$6:$I$23,'S2'!$B$6:$B$23,$A94,'S2'!$E$6:$E$23,"Ambos")+SUMIFS('S3'!$I$6:$I$19,'S3'!$B$6:$B$19,$A94,'S3'!$E$6:$E$19,"Diego")+SUMIFS('S3'!$I$6:$I$19,'S3'!$B$6:$B$19,$A94,'S3'!$E$6:$E$19,"Ambos")+SUMIFS('S4'!$I$6:$I$20,'S4'!$B$6:$B$20,$A94,'S4'!$E$6:$E$20,"Diego")+SUMIFS('S4'!$I$6:$I$20,'S4'!$B$6:$B$20,$A94,'S4'!$E$6:$E$20,"Ambos")+SUMIFS('S5'!$I$6:$I$20,'S5'!$B$6:$B$20,$A94,'S5'!$E$6:$E$20,"Diego")+SUMIFS('S5'!$I$6:$I$20,'S5'!$B$6:$B$20,$A94,'S5'!$E$6:$E$20,"Ambos")+SUMIFS('S6'!$I$6:$I$17,'S6'!$B$6:$B$17,$A94,'S6'!$E$6:$E$17,"Diego")+SUMIFS('S6'!$I$6:$I$17,'S6'!$B$6:$B$17,$A94,'S6'!$E$6:$E$17,"Ambos")+SUMIFS('S7'!$I$6:$I$19,'S7'!$B$6:$B$19,$A94,'S7'!$E$6:$E$19,"Diego")+SUMIFS('S7'!$I$6:$I$19,'S7'!$B$6:$B$19,$A94,'S7'!$E$6:$E$19,"Ambos")+SUMIFS('S8'!$I$6:$I$23,'S8'!$B$6:$B$23,$A94,'S8'!$E$6:$E$23,"Diego")+SUMIFS('S8'!$I$6:$I$23,'S8'!$B$6:$B$23,$A94,'S8'!$E$6:$E$23,"Ambos")+SUMIFS('S9'!$I$6:$I$15,'S9'!$B$6:$B$15,$A94,'S9'!$E$6:$E$15,"Diego")+SUMIFS('S9'!$I$6:$I$15,'S9'!$B$6:$B$15,$A94,'S9'!$E$6:$E$15,"Ambos")+SUMIFS('S10'!$I$6:$I$13,'S10'!$B$6:$B$13,$A94,'S10'!$E$6:$E$13,"Diego")+SUMIFS('S10'!$I$6:$I$13,'S10'!$B$6:$B$13,$A94,'S10'!$E$6:$E$13,"Ambos")+SUMIFS('Holgura'!$I$6:$I$11,'Holgura'!$B$6:$B$11,$A94,'Holgura'!$E$6:$E$11,"Diego")+SUMIFS('Holgura'!$I$6:$I$11,'Holgura'!$B$6:$B$11,$A94,'Holgura'!$E$6:$E$11,"Ambos")+SUMIFS('Entrega'!$I$6:$I$9,'Entrega'!$B$6:$B$9,$A94,'Entrega'!$E$6:$E$9,"Diego")+SUMIFS('Entrega'!$I$6:$I$9,'Entrega'!$B$6:$B$9,$A94,'Entrega'!$E$6:$E$9,"Ambos")+SUMIFS('Defensa'!$I$6:$I$10,'Defensa'!$B$6:$B$10,$A94,'Defensa'!$E$6:$E$10,"Diego")+SUMIFS('Defensa'!$I$6:$I$10,'Defensa'!$B$6:$B$10,$A94,'Defensa'!$E$6:$E$10,"Ambos")</f>
+        <f>SUMIFS('S1'!$I$6:$I$32,'S1'!$B$6:$B$32,$A94,'S1'!$E$6:$E$32,"Diego")+SUMIFS('S1'!$I$6:$I$32,'S1'!$B$6:$B$32,$A94,'S1'!$E$6:$E$32,"Ambos")+SUMIFS('S2'!$I$6:$I$23,'S2'!$B$6:$B$23,$A94,'S2'!$E$6:$E$23,"Diego")+SUMIFS('S2'!$I$6:$I$23,'S2'!$B$6:$B$23,$A94,'S2'!$E$6:$E$23,"Ambos")+SUMIFS('S3'!$I$6:$I$24,'S3'!$B$6:$B$24,$A94,'S3'!$E$6:$E$24,"Diego")+SUMIFS('S3'!$I$6:$I$24,'S3'!$B$6:$B$24,$A94,'S3'!$E$6:$E$24,"Ambos")+SUMIFS('S4'!$I$6:$I$22,'S4'!$B$6:$B$22,$A94,'S4'!$E$6:$E$22,"Diego")+SUMIFS('S4'!$I$6:$I$22,'S4'!$B$6:$B$22,$A94,'S4'!$E$6:$E$22,"Ambos")+SUMIFS('S5'!$I$6:$I$20,'S5'!$B$6:$B$20,$A94,'S5'!$E$6:$E$20,"Diego")+SUMIFS('S5'!$I$6:$I$20,'S5'!$B$6:$B$20,$A94,'S5'!$E$6:$E$20,"Ambos")+SUMIFS('S6'!$I$6:$I$17,'S6'!$B$6:$B$17,$A94,'S6'!$E$6:$E$17,"Diego")+SUMIFS('S6'!$I$6:$I$17,'S6'!$B$6:$B$17,$A94,'S6'!$E$6:$E$17,"Ambos")+SUMIFS('S7'!$I$6:$I$19,'S7'!$B$6:$B$19,$A94,'S7'!$E$6:$E$19,"Diego")+SUMIFS('S7'!$I$6:$I$19,'S7'!$B$6:$B$19,$A94,'S7'!$E$6:$E$19,"Ambos")+SUMIFS('S8'!$I$6:$I$23,'S8'!$B$6:$B$23,$A94,'S8'!$E$6:$E$23,"Diego")+SUMIFS('S8'!$I$6:$I$23,'S8'!$B$6:$B$23,$A94,'S8'!$E$6:$E$23,"Ambos")+SUMIFS('S9'!$I$6:$I$15,'S9'!$B$6:$B$15,$A94,'S9'!$E$6:$E$15,"Diego")+SUMIFS('S9'!$I$6:$I$15,'S9'!$B$6:$B$15,$A94,'S9'!$E$6:$E$15,"Ambos")+SUMIFS('S10'!$I$6:$I$13,'S10'!$B$6:$B$13,$A94,'S10'!$E$6:$E$13,"Diego")+SUMIFS('S10'!$I$6:$I$13,'S10'!$B$6:$B$13,$A94,'S10'!$E$6:$E$13,"Ambos")+SUMIFS('Holgura'!$I$6:$I$11,'Holgura'!$B$6:$B$11,$A94,'Holgura'!$E$6:$E$11,"Diego")+SUMIFS('Holgura'!$I$6:$I$11,'Holgura'!$B$6:$B$11,$A94,'Holgura'!$E$6:$E$11,"Ambos")+SUMIFS('Entrega'!$I$6:$I$9,'Entrega'!$B$6:$B$9,$A94,'Entrega'!$E$6:$E$9,"Diego")+SUMIFS('Entrega'!$I$6:$I$9,'Entrega'!$B$6:$B$9,$A94,'Entrega'!$E$6:$E$9,"Ambos")+SUMIFS('Defensa'!$I$6:$I$10,'Defensa'!$B$6:$B$10,$A94,'Defensa'!$E$6:$E$10,"Diego")+SUMIFS('Defensa'!$I$6:$I$10,'Defensa'!$B$6:$B$10,$A94,'Defensa'!$E$6:$E$10,"Ambos")</f>
         <v/>
       </c>
       <c r="F94" s="21">
-        <f>COUNTIFS('S1'!$B$6:$B$32,$A94,'S1'!$E$6:$E$32,"Víctor")+COUNTIFS('S1'!$B$6:$B$32,$A94,'S1'!$E$6:$E$32,"Ambos")+COUNTIFS('S2'!$B$6:$B$23,$A94,'S2'!$E$6:$E$23,"Víctor")+COUNTIFS('S2'!$B$6:$B$23,$A94,'S2'!$E$6:$E$23,"Ambos")+COUNTIFS('S3'!$B$6:$B$19,$A94,'S3'!$E$6:$E$19,"Víctor")+COUNTIFS('S3'!$B$6:$B$19,$A94,'S3'!$E$6:$E$19,"Ambos")+COUNTIFS('S4'!$B$6:$B$20,$A94,'S4'!$E$6:$E$20,"Víctor")+COUNTIFS('S4'!$B$6:$B$20,$A94,'S4'!$E$6:$E$20,"Ambos")+COUNTIFS('S5'!$B$6:$B$20,$A94,'S5'!$E$6:$E$20,"Víctor")+COUNTIFS('S5'!$B$6:$B$20,$A94,'S5'!$E$6:$E$20,"Ambos")+COUNTIFS('S6'!$B$6:$B$17,$A94,'S6'!$E$6:$E$17,"Víctor")+COUNTIFS('S6'!$B$6:$B$17,$A94,'S6'!$E$6:$E$17,"Ambos")+COUNTIFS('S7'!$B$6:$B$19,$A94,'S7'!$E$6:$E$19,"Víctor")+COUNTIFS('S7'!$B$6:$B$19,$A94,'S7'!$E$6:$E$19,"Ambos")+COUNTIFS('S8'!$B$6:$B$23,$A94,'S8'!$E$6:$E$23,"Víctor")+COUNTIFS('S8'!$B$6:$B$23,$A94,'S8'!$E$6:$E$23,"Ambos")+COUNTIFS('S9'!$B$6:$B$15,$A94,'S9'!$E$6:$E$15,"Víctor")+COUNTIFS('S9'!$B$6:$B$15,$A94,'S9'!$E$6:$E$15,"Ambos")+COUNTIFS('S10'!$B$6:$B$13,$A94,'S10'!$E$6:$E$13,"Víctor")+COUNTIFS('S10'!$B$6:$B$13,$A94,'S10'!$E$6:$E$13,"Ambos")+COUNTIFS('Holgura'!$B$6:$B$11,$A94,'Holgura'!$E$6:$E$11,"Víctor")+COUNTIFS('Holgura'!$B$6:$B$11,$A94,'Holgura'!$E$6:$E$11,"Ambos")+COUNTIFS('Entrega'!$B$6:$B$9,$A94,'Entrega'!$E$6:$E$9,"Víctor")+COUNTIFS('Entrega'!$B$6:$B$9,$A94,'Entrega'!$E$6:$E$9,"Ambos")+COUNTIFS('Defensa'!$B$6:$B$10,$A94,'Defensa'!$E$6:$E$10,"Víctor")+COUNTIFS('Defensa'!$B$6:$B$10,$A94,'Defensa'!$E$6:$E$10,"Ambos")</f>
+        <f>COUNTIFS('S1'!$B$6:$B$32,$A94,'S1'!$E$6:$E$32,"Víctor")+COUNTIFS('S1'!$B$6:$B$32,$A94,'S1'!$E$6:$E$32,"Ambos")+COUNTIFS('S2'!$B$6:$B$23,$A94,'S2'!$E$6:$E$23,"Víctor")+COUNTIFS('S2'!$B$6:$B$23,$A94,'S2'!$E$6:$E$23,"Ambos")+COUNTIFS('S3'!$B$6:$B$24,$A94,'S3'!$E$6:$E$24,"Víctor")+COUNTIFS('S3'!$B$6:$B$24,$A94,'S3'!$E$6:$E$24,"Ambos")+COUNTIFS('S4'!$B$6:$B$22,$A94,'S4'!$E$6:$E$22,"Víctor")+COUNTIFS('S4'!$B$6:$B$22,$A94,'S4'!$E$6:$E$22,"Ambos")+COUNTIFS('S5'!$B$6:$B$20,$A94,'S5'!$E$6:$E$20,"Víctor")+COUNTIFS('S5'!$B$6:$B$20,$A94,'S5'!$E$6:$E$20,"Ambos")+COUNTIFS('S6'!$B$6:$B$17,$A94,'S6'!$E$6:$E$17,"Víctor")+COUNTIFS('S6'!$B$6:$B$17,$A94,'S6'!$E$6:$E$17,"Ambos")+COUNTIFS('S7'!$B$6:$B$19,$A94,'S7'!$E$6:$E$19,"Víctor")+COUNTIFS('S7'!$B$6:$B$19,$A94,'S7'!$E$6:$E$19,"Ambos")+COUNTIFS('S8'!$B$6:$B$23,$A94,'S8'!$E$6:$E$23,"Víctor")+COUNTIFS('S8'!$B$6:$B$23,$A94,'S8'!$E$6:$E$23,"Ambos")+COUNTIFS('S9'!$B$6:$B$15,$A94,'S9'!$E$6:$E$15,"Víctor")+COUNTIFS('S9'!$B$6:$B$15,$A94,'S9'!$E$6:$E$15,"Ambos")+COUNTIFS('S10'!$B$6:$B$13,$A94,'S10'!$E$6:$E$13,"Víctor")+COUNTIFS('S10'!$B$6:$B$13,$A94,'S10'!$E$6:$E$13,"Ambos")+COUNTIFS('Holgura'!$B$6:$B$11,$A94,'Holgura'!$E$6:$E$11,"Víctor")+COUNTIFS('Holgura'!$B$6:$B$11,$A94,'Holgura'!$E$6:$E$11,"Ambos")+COUNTIFS('Entrega'!$B$6:$B$9,$A94,'Entrega'!$E$6:$E$9,"Víctor")+COUNTIFS('Entrega'!$B$6:$B$9,$A94,'Entrega'!$E$6:$E$9,"Ambos")+COUNTIFS('Defensa'!$B$6:$B$10,$A94,'Defensa'!$E$6:$E$10,"Víctor")+COUNTIFS('Defensa'!$B$6:$B$10,$A94,'Defensa'!$E$6:$E$10,"Ambos")</f>
         <v/>
       </c>
       <c r="G94" s="21">
-        <f>COUNTIFS('S1'!$B$6:$B$32,$A94,'S1'!$E$6:$E$32,"Diego")+COUNTIFS('S1'!$B$6:$B$32,$A94,'S1'!$E$6:$E$32,"Ambos")+COUNTIFS('S2'!$B$6:$B$23,$A94,'S2'!$E$6:$E$23,"Diego")+COUNTIFS('S2'!$B$6:$B$23,$A94,'S2'!$E$6:$E$23,"Ambos")+COUNTIFS('S3'!$B$6:$B$19,$A94,'S3'!$E$6:$E$19,"Diego")+COUNTIFS('S3'!$B$6:$B$19,$A94,'S3'!$E$6:$E$19,"Ambos")+COUNTIFS('S4'!$B$6:$B$20,$A94,'S4'!$E$6:$E$20,"Diego")+COUNTIFS('S4'!$B$6:$B$20,$A94,'S4'!$E$6:$E$20,"Ambos")+COUNTIFS('S5'!$B$6:$B$20,$A94,'S5'!$E$6:$E$20,"Diego")+COUNTIFS('S5'!$B$6:$B$20,$A94,'S5'!$E$6:$E$20,"Ambos")+COUNTIFS('S6'!$B$6:$B$17,$A94,'S6'!$E$6:$E$17,"Diego")+COUNTIFS('S6'!$B$6:$B$17,$A94,'S6'!$E$6:$E$17,"Ambos")+COUNTIFS('S7'!$B$6:$B$19,$A94,'S7'!$E$6:$E$19,"Diego")+COUNTIFS('S7'!$B$6:$B$19,$A94,'S7'!$E$6:$E$19,"Ambos")+COUNTIFS('S8'!$B$6:$B$23,$A94,'S8'!$E$6:$E$23,"Diego")+COUNTIFS('S8'!$B$6:$B$23,$A94,'S8'!$E$6:$E$23,"Ambos")+COUNTIFS('S9'!$B$6:$B$15,$A94,'S9'!$E$6:$E$15,"Diego")+COUNTIFS('S9'!$B$6:$B$15,$A94,'S9'!$E$6:$E$15,"Ambos")+COUNTIFS('S10'!$B$6:$B$13,$A94,'S10'!$E$6:$E$13,"Diego")+COUNTIFS('S10'!$B$6:$B$13,$A94,'S10'!$E$6:$E$13,"Ambos")+COUNTIFS('Holgura'!$B$6:$B$11,$A94,'Holgura'!$E$6:$E$11,"Diego")+COUNTIFS('Holgura'!$B$6:$B$11,$A94,'Holgura'!$E$6:$E$11,"Ambos")+COUNTIFS('Entrega'!$B$6:$B$9,$A94,'Entrega'!$E$6:$E$9,"Diego")+COUNTIFS('Entrega'!$B$6:$B$9,$A94,'Entrega'!$E$6:$E$9,"Ambos")+COUNTIFS('Defensa'!$B$6:$B$10,$A94,'Defensa'!$E$6:$E$10,"Diego")+COUNTIFS('Defensa'!$B$6:$B$10,$A94,'Defensa'!$E$6:$E$10,"Ambos")</f>
+        <f>COUNTIFS('S1'!$B$6:$B$32,$A94,'S1'!$E$6:$E$32,"Diego")+COUNTIFS('S1'!$B$6:$B$32,$A94,'S1'!$E$6:$E$32,"Ambos")+COUNTIFS('S2'!$B$6:$B$23,$A94,'S2'!$E$6:$E$23,"Diego")+COUNTIFS('S2'!$B$6:$B$23,$A94,'S2'!$E$6:$E$23,"Ambos")+COUNTIFS('S3'!$B$6:$B$24,$A94,'S3'!$E$6:$E$24,"Diego")+COUNTIFS('S3'!$B$6:$B$24,$A94,'S3'!$E$6:$E$24,"Ambos")+COUNTIFS('S4'!$B$6:$B$22,$A94,'S4'!$E$6:$E$22,"Diego")+COUNTIFS('S4'!$B$6:$B$22,$A94,'S4'!$E$6:$E$22,"Ambos")+COUNTIFS('S5'!$B$6:$B$20,$A94,'S5'!$E$6:$E$20,"Diego")+COUNTIFS('S5'!$B$6:$B$20,$A94,'S5'!$E$6:$E$20,"Ambos")+COUNTIFS('S6'!$B$6:$B$17,$A94,'S6'!$E$6:$E$17,"Diego")+COUNTIFS('S6'!$B$6:$B$17,$A94,'S6'!$E$6:$E$17,"Ambos")+COUNTIFS('S7'!$B$6:$B$19,$A94,'S7'!$E$6:$E$19,"Diego")+COUNTIFS('S7'!$B$6:$B$19,$A94,'S7'!$E$6:$E$19,"Ambos")+COUNTIFS('S8'!$B$6:$B$23,$A94,'S8'!$E$6:$E$23,"Diego")+COUNTIFS('S8'!$B$6:$B$23,$A94,'S8'!$E$6:$E$23,"Ambos")+COUNTIFS('S9'!$B$6:$B$15,$A94,'S9'!$E$6:$E$15,"Diego")+COUNTIFS('S9'!$B$6:$B$15,$A94,'S9'!$E$6:$E$15,"Ambos")+COUNTIFS('S10'!$B$6:$B$13,$A94,'S10'!$E$6:$E$13,"Diego")+COUNTIFS('S10'!$B$6:$B$13,$A94,'S10'!$E$6:$E$13,"Ambos")+COUNTIFS('Holgura'!$B$6:$B$11,$A94,'Holgura'!$E$6:$E$11,"Diego")+COUNTIFS('Holgura'!$B$6:$B$11,$A94,'Holgura'!$E$6:$E$11,"Ambos")+COUNTIFS('Entrega'!$B$6:$B$9,$A94,'Entrega'!$E$6:$E$9,"Diego")+COUNTIFS('Entrega'!$B$6:$B$9,$A94,'Entrega'!$E$6:$E$9,"Ambos")+COUNTIFS('Defensa'!$B$6:$B$10,$A94,'Defensa'!$E$6:$E$10,"Diego")+COUNTIFS('Defensa'!$B$6:$B$10,$A94,'Defensa'!$E$6:$E$10,"Ambos")</f>
         <v/>
       </c>
     </row>
@@ -11290,19 +11311,19 @@
         <v/>
       </c>
       <c r="D95" s="21">
-        <f>SUMIFS('S1'!$I$6:$I$32,'S1'!$B$6:$B$32,$A95,'S1'!$E$6:$E$32,"Víctor")+SUMIFS('S1'!$I$6:$I$32,'S1'!$B$6:$B$32,$A95,'S1'!$E$6:$E$32,"Ambos")+SUMIFS('S2'!$I$6:$I$23,'S2'!$B$6:$B$23,$A95,'S2'!$E$6:$E$23,"Víctor")+SUMIFS('S2'!$I$6:$I$23,'S2'!$B$6:$B$23,$A95,'S2'!$E$6:$E$23,"Ambos")+SUMIFS('S3'!$I$6:$I$19,'S3'!$B$6:$B$19,$A95,'S3'!$E$6:$E$19,"Víctor")+SUMIFS('S3'!$I$6:$I$19,'S3'!$B$6:$B$19,$A95,'S3'!$E$6:$E$19,"Ambos")+SUMIFS('S4'!$I$6:$I$20,'S4'!$B$6:$B$20,$A95,'S4'!$E$6:$E$20,"Víctor")+SUMIFS('S4'!$I$6:$I$20,'S4'!$B$6:$B$20,$A95,'S4'!$E$6:$E$20,"Ambos")+SUMIFS('S5'!$I$6:$I$20,'S5'!$B$6:$B$20,$A95,'S5'!$E$6:$E$20,"Víctor")+SUMIFS('S5'!$I$6:$I$20,'S5'!$B$6:$B$20,$A95,'S5'!$E$6:$E$20,"Ambos")+SUMIFS('S6'!$I$6:$I$17,'S6'!$B$6:$B$17,$A95,'S6'!$E$6:$E$17,"Víctor")+SUMIFS('S6'!$I$6:$I$17,'S6'!$B$6:$B$17,$A95,'S6'!$E$6:$E$17,"Ambos")+SUMIFS('S7'!$I$6:$I$19,'S7'!$B$6:$B$19,$A95,'S7'!$E$6:$E$19,"Víctor")+SUMIFS('S7'!$I$6:$I$19,'S7'!$B$6:$B$19,$A95,'S7'!$E$6:$E$19,"Ambos")+SUMIFS('S8'!$I$6:$I$23,'S8'!$B$6:$B$23,$A95,'S8'!$E$6:$E$23,"Víctor")+SUMIFS('S8'!$I$6:$I$23,'S8'!$B$6:$B$23,$A95,'S8'!$E$6:$E$23,"Ambos")+SUMIFS('S9'!$I$6:$I$15,'S9'!$B$6:$B$15,$A95,'S9'!$E$6:$E$15,"Víctor")+SUMIFS('S9'!$I$6:$I$15,'S9'!$B$6:$B$15,$A95,'S9'!$E$6:$E$15,"Ambos")+SUMIFS('S10'!$I$6:$I$13,'S10'!$B$6:$B$13,$A95,'S10'!$E$6:$E$13,"Víctor")+SUMIFS('S10'!$I$6:$I$13,'S10'!$B$6:$B$13,$A95,'S10'!$E$6:$E$13,"Ambos")+SUMIFS('Holgura'!$I$6:$I$11,'Holgura'!$B$6:$B$11,$A95,'Holgura'!$E$6:$E$11,"Víctor")+SUMIFS('Holgura'!$I$6:$I$11,'Holgura'!$B$6:$B$11,$A95,'Holgura'!$E$6:$E$11,"Ambos")+SUMIFS('Entrega'!$I$6:$I$9,'Entrega'!$B$6:$B$9,$A95,'Entrega'!$E$6:$E$9,"Víctor")+SUMIFS('Entrega'!$I$6:$I$9,'Entrega'!$B$6:$B$9,$A95,'Entrega'!$E$6:$E$9,"Ambos")+SUMIFS('Defensa'!$I$6:$I$10,'Defensa'!$B$6:$B$10,$A95,'Defensa'!$E$6:$E$10,"Víctor")+SUMIFS('Defensa'!$I$6:$I$10,'Defensa'!$B$6:$B$10,$A95,'Defensa'!$E$6:$E$10,"Ambos")</f>
+        <f>SUMIFS('S1'!$I$6:$I$32,'S1'!$B$6:$B$32,$A95,'S1'!$E$6:$E$32,"Víctor")+SUMIFS('S1'!$I$6:$I$32,'S1'!$B$6:$B$32,$A95,'S1'!$E$6:$E$32,"Ambos")+SUMIFS('S2'!$I$6:$I$23,'S2'!$B$6:$B$23,$A95,'S2'!$E$6:$E$23,"Víctor")+SUMIFS('S2'!$I$6:$I$23,'S2'!$B$6:$B$23,$A95,'S2'!$E$6:$E$23,"Ambos")+SUMIFS('S3'!$I$6:$I$24,'S3'!$B$6:$B$24,$A95,'S3'!$E$6:$E$24,"Víctor")+SUMIFS('S3'!$I$6:$I$24,'S3'!$B$6:$B$24,$A95,'S3'!$E$6:$E$24,"Ambos")+SUMIFS('S4'!$I$6:$I$22,'S4'!$B$6:$B$22,$A95,'S4'!$E$6:$E$22,"Víctor")+SUMIFS('S4'!$I$6:$I$22,'S4'!$B$6:$B$22,$A95,'S4'!$E$6:$E$22,"Ambos")+SUMIFS('S5'!$I$6:$I$20,'S5'!$B$6:$B$20,$A95,'S5'!$E$6:$E$20,"Víctor")+SUMIFS('S5'!$I$6:$I$20,'S5'!$B$6:$B$20,$A95,'S5'!$E$6:$E$20,"Ambos")+SUMIFS('S6'!$I$6:$I$17,'S6'!$B$6:$B$17,$A95,'S6'!$E$6:$E$17,"Víctor")+SUMIFS('S6'!$I$6:$I$17,'S6'!$B$6:$B$17,$A95,'S6'!$E$6:$E$17,"Ambos")+SUMIFS('S7'!$I$6:$I$19,'S7'!$B$6:$B$19,$A95,'S7'!$E$6:$E$19,"Víctor")+SUMIFS('S7'!$I$6:$I$19,'S7'!$B$6:$B$19,$A95,'S7'!$E$6:$E$19,"Ambos")+SUMIFS('S8'!$I$6:$I$23,'S8'!$B$6:$B$23,$A95,'S8'!$E$6:$E$23,"Víctor")+SUMIFS('S8'!$I$6:$I$23,'S8'!$B$6:$B$23,$A95,'S8'!$E$6:$E$23,"Ambos")+SUMIFS('S9'!$I$6:$I$15,'S9'!$B$6:$B$15,$A95,'S9'!$E$6:$E$15,"Víctor")+SUMIFS('S9'!$I$6:$I$15,'S9'!$B$6:$B$15,$A95,'S9'!$E$6:$E$15,"Ambos")+SUMIFS('S10'!$I$6:$I$13,'S10'!$B$6:$B$13,$A95,'S10'!$E$6:$E$13,"Víctor")+SUMIFS('S10'!$I$6:$I$13,'S10'!$B$6:$B$13,$A95,'S10'!$E$6:$E$13,"Ambos")+SUMIFS('Holgura'!$I$6:$I$11,'Holgura'!$B$6:$B$11,$A95,'Holgura'!$E$6:$E$11,"Víctor")+SUMIFS('Holgura'!$I$6:$I$11,'Holgura'!$B$6:$B$11,$A95,'Holgura'!$E$6:$E$11,"Ambos")+SUMIFS('Entrega'!$I$6:$I$9,'Entrega'!$B$6:$B$9,$A95,'Entrega'!$E$6:$E$9,"Víctor")+SUMIFS('Entrega'!$I$6:$I$9,'Entrega'!$B$6:$B$9,$A95,'Entrega'!$E$6:$E$9,"Ambos")+SUMIFS('Defensa'!$I$6:$I$10,'Defensa'!$B$6:$B$10,$A95,'Defensa'!$E$6:$E$10,"Víctor")+SUMIFS('Defensa'!$I$6:$I$10,'Defensa'!$B$6:$B$10,$A95,'Defensa'!$E$6:$E$10,"Ambos")</f>
         <v/>
       </c>
       <c r="E95" s="21">
-        <f>SUMIFS('S1'!$I$6:$I$32,'S1'!$B$6:$B$32,$A95,'S1'!$E$6:$E$32,"Diego")+SUMIFS('S1'!$I$6:$I$32,'S1'!$B$6:$B$32,$A95,'S1'!$E$6:$E$32,"Ambos")+SUMIFS('S2'!$I$6:$I$23,'S2'!$B$6:$B$23,$A95,'S2'!$E$6:$E$23,"Diego")+SUMIFS('S2'!$I$6:$I$23,'S2'!$B$6:$B$23,$A95,'S2'!$E$6:$E$23,"Ambos")+SUMIFS('S3'!$I$6:$I$19,'S3'!$B$6:$B$19,$A95,'S3'!$E$6:$E$19,"Diego")+SUMIFS('S3'!$I$6:$I$19,'S3'!$B$6:$B$19,$A95,'S3'!$E$6:$E$19,"Ambos")+SUMIFS('S4'!$I$6:$I$20,'S4'!$B$6:$B$20,$A95,'S4'!$E$6:$E$20,"Diego")+SUMIFS('S4'!$I$6:$I$20,'S4'!$B$6:$B$20,$A95,'S4'!$E$6:$E$20,"Ambos")+SUMIFS('S5'!$I$6:$I$20,'S5'!$B$6:$B$20,$A95,'S5'!$E$6:$E$20,"Diego")+SUMIFS('S5'!$I$6:$I$20,'S5'!$B$6:$B$20,$A95,'S5'!$E$6:$E$20,"Ambos")+SUMIFS('S6'!$I$6:$I$17,'S6'!$B$6:$B$17,$A95,'S6'!$E$6:$E$17,"Diego")+SUMIFS('S6'!$I$6:$I$17,'S6'!$B$6:$B$17,$A95,'S6'!$E$6:$E$17,"Ambos")+SUMIFS('S7'!$I$6:$I$19,'S7'!$B$6:$B$19,$A95,'S7'!$E$6:$E$19,"Diego")+SUMIFS('S7'!$I$6:$I$19,'S7'!$B$6:$B$19,$A95,'S7'!$E$6:$E$19,"Ambos")+SUMIFS('S8'!$I$6:$I$23,'S8'!$B$6:$B$23,$A95,'S8'!$E$6:$E$23,"Diego")+SUMIFS('S8'!$I$6:$I$23,'S8'!$B$6:$B$23,$A95,'S8'!$E$6:$E$23,"Ambos")+SUMIFS('S9'!$I$6:$I$15,'S9'!$B$6:$B$15,$A95,'S9'!$E$6:$E$15,"Diego")+SUMIFS('S9'!$I$6:$I$15,'S9'!$B$6:$B$15,$A95,'S9'!$E$6:$E$15,"Ambos")+SUMIFS('S10'!$I$6:$I$13,'S10'!$B$6:$B$13,$A95,'S10'!$E$6:$E$13,"Diego")+SUMIFS('S10'!$I$6:$I$13,'S10'!$B$6:$B$13,$A95,'S10'!$E$6:$E$13,"Ambos")+SUMIFS('Holgura'!$I$6:$I$11,'Holgura'!$B$6:$B$11,$A95,'Holgura'!$E$6:$E$11,"Diego")+SUMIFS('Holgura'!$I$6:$I$11,'Holgura'!$B$6:$B$11,$A95,'Holgura'!$E$6:$E$11,"Ambos")+SUMIFS('Entrega'!$I$6:$I$9,'Entrega'!$B$6:$B$9,$A95,'Entrega'!$E$6:$E$9,"Diego")+SUMIFS('Entrega'!$I$6:$I$9,'Entrega'!$B$6:$B$9,$A95,'Entrega'!$E$6:$E$9,"Ambos")+SUMIFS('Defensa'!$I$6:$I$10,'Defensa'!$B$6:$B$10,$A95,'Defensa'!$E$6:$E$10,"Diego")+SUMIFS('Defensa'!$I$6:$I$10,'Defensa'!$B$6:$B$10,$A95,'Defensa'!$E$6:$E$10,"Ambos")</f>
+        <f>SUMIFS('S1'!$I$6:$I$32,'S1'!$B$6:$B$32,$A95,'S1'!$E$6:$E$32,"Diego")+SUMIFS('S1'!$I$6:$I$32,'S1'!$B$6:$B$32,$A95,'S1'!$E$6:$E$32,"Ambos")+SUMIFS('S2'!$I$6:$I$23,'S2'!$B$6:$B$23,$A95,'S2'!$E$6:$E$23,"Diego")+SUMIFS('S2'!$I$6:$I$23,'S2'!$B$6:$B$23,$A95,'S2'!$E$6:$E$23,"Ambos")+SUMIFS('S3'!$I$6:$I$24,'S3'!$B$6:$B$24,$A95,'S3'!$E$6:$E$24,"Diego")+SUMIFS('S3'!$I$6:$I$24,'S3'!$B$6:$B$24,$A95,'S3'!$E$6:$E$24,"Ambos")+SUMIFS('S4'!$I$6:$I$22,'S4'!$B$6:$B$22,$A95,'S4'!$E$6:$E$22,"Diego")+SUMIFS('S4'!$I$6:$I$22,'S4'!$B$6:$B$22,$A95,'S4'!$E$6:$E$22,"Ambos")+SUMIFS('S5'!$I$6:$I$20,'S5'!$B$6:$B$20,$A95,'S5'!$E$6:$E$20,"Diego")+SUMIFS('S5'!$I$6:$I$20,'S5'!$B$6:$B$20,$A95,'S5'!$E$6:$E$20,"Ambos")+SUMIFS('S6'!$I$6:$I$17,'S6'!$B$6:$B$17,$A95,'S6'!$E$6:$E$17,"Diego")+SUMIFS('S6'!$I$6:$I$17,'S6'!$B$6:$B$17,$A95,'S6'!$E$6:$E$17,"Ambos")+SUMIFS('S7'!$I$6:$I$19,'S7'!$B$6:$B$19,$A95,'S7'!$E$6:$E$19,"Diego")+SUMIFS('S7'!$I$6:$I$19,'S7'!$B$6:$B$19,$A95,'S7'!$E$6:$E$19,"Ambos")+SUMIFS('S8'!$I$6:$I$23,'S8'!$B$6:$B$23,$A95,'S8'!$E$6:$E$23,"Diego")+SUMIFS('S8'!$I$6:$I$23,'S8'!$B$6:$B$23,$A95,'S8'!$E$6:$E$23,"Ambos")+SUMIFS('S9'!$I$6:$I$15,'S9'!$B$6:$B$15,$A95,'S9'!$E$6:$E$15,"Diego")+SUMIFS('S9'!$I$6:$I$15,'S9'!$B$6:$B$15,$A95,'S9'!$E$6:$E$15,"Ambos")+SUMIFS('S10'!$I$6:$I$13,'S10'!$B$6:$B$13,$A95,'S10'!$E$6:$E$13,"Diego")+SUMIFS('S10'!$I$6:$I$13,'S10'!$B$6:$B$13,$A95,'S10'!$E$6:$E$13,"Ambos")+SUMIFS('Holgura'!$I$6:$I$11,'Holgura'!$B$6:$B$11,$A95,'Holgura'!$E$6:$E$11,"Diego")+SUMIFS('Holgura'!$I$6:$I$11,'Holgura'!$B$6:$B$11,$A95,'Holgura'!$E$6:$E$11,"Ambos")+SUMIFS('Entrega'!$I$6:$I$9,'Entrega'!$B$6:$B$9,$A95,'Entrega'!$E$6:$E$9,"Diego")+SUMIFS('Entrega'!$I$6:$I$9,'Entrega'!$B$6:$B$9,$A95,'Entrega'!$E$6:$E$9,"Ambos")+SUMIFS('Defensa'!$I$6:$I$10,'Defensa'!$B$6:$B$10,$A95,'Defensa'!$E$6:$E$10,"Diego")+SUMIFS('Defensa'!$I$6:$I$10,'Defensa'!$B$6:$B$10,$A95,'Defensa'!$E$6:$E$10,"Ambos")</f>
         <v/>
       </c>
       <c r="F95" s="21">
-        <f>COUNTIFS('S1'!$B$6:$B$32,$A95,'S1'!$E$6:$E$32,"Víctor")+COUNTIFS('S1'!$B$6:$B$32,$A95,'S1'!$E$6:$E$32,"Ambos")+COUNTIFS('S2'!$B$6:$B$23,$A95,'S2'!$E$6:$E$23,"Víctor")+COUNTIFS('S2'!$B$6:$B$23,$A95,'S2'!$E$6:$E$23,"Ambos")+COUNTIFS('S3'!$B$6:$B$19,$A95,'S3'!$E$6:$E$19,"Víctor")+COUNTIFS('S3'!$B$6:$B$19,$A95,'S3'!$E$6:$E$19,"Ambos")+COUNTIFS('S4'!$B$6:$B$20,$A95,'S4'!$E$6:$E$20,"Víctor")+COUNTIFS('S4'!$B$6:$B$20,$A95,'S4'!$E$6:$E$20,"Ambos")+COUNTIFS('S5'!$B$6:$B$20,$A95,'S5'!$E$6:$E$20,"Víctor")+COUNTIFS('S5'!$B$6:$B$20,$A95,'S5'!$E$6:$E$20,"Ambos")+COUNTIFS('S6'!$B$6:$B$17,$A95,'S6'!$E$6:$E$17,"Víctor")+COUNTIFS('S6'!$B$6:$B$17,$A95,'S6'!$E$6:$E$17,"Ambos")+COUNTIFS('S7'!$B$6:$B$19,$A95,'S7'!$E$6:$E$19,"Víctor")+COUNTIFS('S7'!$B$6:$B$19,$A95,'S7'!$E$6:$E$19,"Ambos")+COUNTIFS('S8'!$B$6:$B$23,$A95,'S8'!$E$6:$E$23,"Víctor")+COUNTIFS('S8'!$B$6:$B$23,$A95,'S8'!$E$6:$E$23,"Ambos")+COUNTIFS('S9'!$B$6:$B$15,$A95,'S9'!$E$6:$E$15,"Víctor")+COUNTIFS('S9'!$B$6:$B$15,$A95,'S9'!$E$6:$E$15,"Ambos")+COUNTIFS('S10'!$B$6:$B$13,$A95,'S10'!$E$6:$E$13,"Víctor")+COUNTIFS('S10'!$B$6:$B$13,$A95,'S10'!$E$6:$E$13,"Ambos")+COUNTIFS('Holgura'!$B$6:$B$11,$A95,'Holgura'!$E$6:$E$11,"Víctor")+COUNTIFS('Holgura'!$B$6:$B$11,$A95,'Holgura'!$E$6:$E$11,"Ambos")+COUNTIFS('Entrega'!$B$6:$B$9,$A95,'Entrega'!$E$6:$E$9,"Víctor")+COUNTIFS('Entrega'!$B$6:$B$9,$A95,'Entrega'!$E$6:$E$9,"Ambos")+COUNTIFS('Defensa'!$B$6:$B$10,$A95,'Defensa'!$E$6:$E$10,"Víctor")+COUNTIFS('Defensa'!$B$6:$B$10,$A95,'Defensa'!$E$6:$E$10,"Ambos")</f>
+        <f>COUNTIFS('S1'!$B$6:$B$32,$A95,'S1'!$E$6:$E$32,"Víctor")+COUNTIFS('S1'!$B$6:$B$32,$A95,'S1'!$E$6:$E$32,"Ambos")+COUNTIFS('S2'!$B$6:$B$23,$A95,'S2'!$E$6:$E$23,"Víctor")+COUNTIFS('S2'!$B$6:$B$23,$A95,'S2'!$E$6:$E$23,"Ambos")+COUNTIFS('S3'!$B$6:$B$24,$A95,'S3'!$E$6:$E$24,"Víctor")+COUNTIFS('S3'!$B$6:$B$24,$A95,'S3'!$E$6:$E$24,"Ambos")+COUNTIFS('S4'!$B$6:$B$22,$A95,'S4'!$E$6:$E$22,"Víctor")+COUNTIFS('S4'!$B$6:$B$22,$A95,'S4'!$E$6:$E$22,"Ambos")+COUNTIFS('S5'!$B$6:$B$20,$A95,'S5'!$E$6:$E$20,"Víctor")+COUNTIFS('S5'!$B$6:$B$20,$A95,'S5'!$E$6:$E$20,"Ambos")+COUNTIFS('S6'!$B$6:$B$17,$A95,'S6'!$E$6:$E$17,"Víctor")+COUNTIFS('S6'!$B$6:$B$17,$A95,'S6'!$E$6:$E$17,"Ambos")+COUNTIFS('S7'!$B$6:$B$19,$A95,'S7'!$E$6:$E$19,"Víctor")+COUNTIFS('S7'!$B$6:$B$19,$A95,'S7'!$E$6:$E$19,"Ambos")+COUNTIFS('S8'!$B$6:$B$23,$A95,'S8'!$E$6:$E$23,"Víctor")+COUNTIFS('S8'!$B$6:$B$23,$A95,'S8'!$E$6:$E$23,"Ambos")+COUNTIFS('S9'!$B$6:$B$15,$A95,'S9'!$E$6:$E$15,"Víctor")+COUNTIFS('S9'!$B$6:$B$15,$A95,'S9'!$E$6:$E$15,"Ambos")+COUNTIFS('S10'!$B$6:$B$13,$A95,'S10'!$E$6:$E$13,"Víctor")+COUNTIFS('S10'!$B$6:$B$13,$A95,'S10'!$E$6:$E$13,"Ambos")+COUNTIFS('Holgura'!$B$6:$B$11,$A95,'Holgura'!$E$6:$E$11,"Víctor")+COUNTIFS('Holgura'!$B$6:$B$11,$A95,'Holgura'!$E$6:$E$11,"Ambos")+COUNTIFS('Entrega'!$B$6:$B$9,$A95,'Entrega'!$E$6:$E$9,"Víctor")+COUNTIFS('Entrega'!$B$6:$B$9,$A95,'Entrega'!$E$6:$E$9,"Ambos")+COUNTIFS('Defensa'!$B$6:$B$10,$A95,'Defensa'!$E$6:$E$10,"Víctor")+COUNTIFS('Defensa'!$B$6:$B$10,$A95,'Defensa'!$E$6:$E$10,"Ambos")</f>
         <v/>
       </c>
       <c r="G95" s="21">
-        <f>COUNTIFS('S1'!$B$6:$B$32,$A95,'S1'!$E$6:$E$32,"Diego")+COUNTIFS('S1'!$B$6:$B$32,$A95,'S1'!$E$6:$E$32,"Ambos")+COUNTIFS('S2'!$B$6:$B$23,$A95,'S2'!$E$6:$E$23,"Diego")+COUNTIFS('S2'!$B$6:$B$23,$A95,'S2'!$E$6:$E$23,"Ambos")+COUNTIFS('S3'!$B$6:$B$19,$A95,'S3'!$E$6:$E$19,"Diego")+COUNTIFS('S3'!$B$6:$B$19,$A95,'S3'!$E$6:$E$19,"Ambos")+COUNTIFS('S4'!$B$6:$B$20,$A95,'S4'!$E$6:$E$20,"Diego")+COUNTIFS('S4'!$B$6:$B$20,$A95,'S4'!$E$6:$E$20,"Ambos")+COUNTIFS('S5'!$B$6:$B$20,$A95,'S5'!$E$6:$E$20,"Diego")+COUNTIFS('S5'!$B$6:$B$20,$A95,'S5'!$E$6:$E$20,"Ambos")+COUNTIFS('S6'!$B$6:$B$17,$A95,'S6'!$E$6:$E$17,"Diego")+COUNTIFS('S6'!$B$6:$B$17,$A95,'S6'!$E$6:$E$17,"Ambos")+COUNTIFS('S7'!$B$6:$B$19,$A95,'S7'!$E$6:$E$19,"Diego")+COUNTIFS('S7'!$B$6:$B$19,$A95,'S7'!$E$6:$E$19,"Ambos")+COUNTIFS('S8'!$B$6:$B$23,$A95,'S8'!$E$6:$E$23,"Diego")+COUNTIFS('S8'!$B$6:$B$23,$A95,'S8'!$E$6:$E$23,"Ambos")+COUNTIFS('S9'!$B$6:$B$15,$A95,'S9'!$E$6:$E$15,"Diego")+COUNTIFS('S9'!$B$6:$B$15,$A95,'S9'!$E$6:$E$15,"Ambos")+COUNTIFS('S10'!$B$6:$B$13,$A95,'S10'!$E$6:$E$13,"Diego")+COUNTIFS('S10'!$B$6:$B$13,$A95,'S10'!$E$6:$E$13,"Ambos")+COUNTIFS('Holgura'!$B$6:$B$11,$A95,'Holgura'!$E$6:$E$11,"Diego")+COUNTIFS('Holgura'!$B$6:$B$11,$A95,'Holgura'!$E$6:$E$11,"Ambos")+COUNTIFS('Entrega'!$B$6:$B$9,$A95,'Entrega'!$E$6:$E$9,"Diego")+COUNTIFS('Entrega'!$B$6:$B$9,$A95,'Entrega'!$E$6:$E$9,"Ambos")+COUNTIFS('Defensa'!$B$6:$B$10,$A95,'Defensa'!$E$6:$E$10,"Diego")+COUNTIFS('Defensa'!$B$6:$B$10,$A95,'Defensa'!$E$6:$E$10,"Ambos")</f>
+        <f>COUNTIFS('S1'!$B$6:$B$32,$A95,'S1'!$E$6:$E$32,"Diego")+COUNTIFS('S1'!$B$6:$B$32,$A95,'S1'!$E$6:$E$32,"Ambos")+COUNTIFS('S2'!$B$6:$B$23,$A95,'S2'!$E$6:$E$23,"Diego")+COUNTIFS('S2'!$B$6:$B$23,$A95,'S2'!$E$6:$E$23,"Ambos")+COUNTIFS('S3'!$B$6:$B$24,$A95,'S3'!$E$6:$E$24,"Diego")+COUNTIFS('S3'!$B$6:$B$24,$A95,'S3'!$E$6:$E$24,"Ambos")+COUNTIFS('S4'!$B$6:$B$22,$A95,'S4'!$E$6:$E$22,"Diego")+COUNTIFS('S4'!$B$6:$B$22,$A95,'S4'!$E$6:$E$22,"Ambos")+COUNTIFS('S5'!$B$6:$B$20,$A95,'S5'!$E$6:$E$20,"Diego")+COUNTIFS('S5'!$B$6:$B$20,$A95,'S5'!$E$6:$E$20,"Ambos")+COUNTIFS('S6'!$B$6:$B$17,$A95,'S6'!$E$6:$E$17,"Diego")+COUNTIFS('S6'!$B$6:$B$17,$A95,'S6'!$E$6:$E$17,"Ambos")+COUNTIFS('S7'!$B$6:$B$19,$A95,'S7'!$E$6:$E$19,"Diego")+COUNTIFS('S7'!$B$6:$B$19,$A95,'S7'!$E$6:$E$19,"Ambos")+COUNTIFS('S8'!$B$6:$B$23,$A95,'S8'!$E$6:$E$23,"Diego")+COUNTIFS('S8'!$B$6:$B$23,$A95,'S8'!$E$6:$E$23,"Ambos")+COUNTIFS('S9'!$B$6:$B$15,$A95,'S9'!$E$6:$E$15,"Diego")+COUNTIFS('S9'!$B$6:$B$15,$A95,'S9'!$E$6:$E$15,"Ambos")+COUNTIFS('S10'!$B$6:$B$13,$A95,'S10'!$E$6:$E$13,"Diego")+COUNTIFS('S10'!$B$6:$B$13,$A95,'S10'!$E$6:$E$13,"Ambos")+COUNTIFS('Holgura'!$B$6:$B$11,$A95,'Holgura'!$E$6:$E$11,"Diego")+COUNTIFS('Holgura'!$B$6:$B$11,$A95,'Holgura'!$E$6:$E$11,"Ambos")+COUNTIFS('Entrega'!$B$6:$B$9,$A95,'Entrega'!$E$6:$E$9,"Diego")+COUNTIFS('Entrega'!$B$6:$B$9,$A95,'Entrega'!$E$6:$E$9,"Ambos")+COUNTIFS('Defensa'!$B$6:$B$10,$A95,'Defensa'!$E$6:$E$10,"Diego")+COUNTIFS('Defensa'!$B$6:$B$10,$A95,'Defensa'!$E$6:$E$10,"Ambos")</f>
         <v/>
       </c>
     </row>
@@ -11319,19 +11340,19 @@
         <v/>
       </c>
       <c r="D96" s="21">
-        <f>SUMIFS('S1'!$I$6:$I$32,'S1'!$B$6:$B$32,$A96,'S1'!$E$6:$E$32,"Víctor")+SUMIFS('S1'!$I$6:$I$32,'S1'!$B$6:$B$32,$A96,'S1'!$E$6:$E$32,"Ambos")+SUMIFS('S2'!$I$6:$I$23,'S2'!$B$6:$B$23,$A96,'S2'!$E$6:$E$23,"Víctor")+SUMIFS('S2'!$I$6:$I$23,'S2'!$B$6:$B$23,$A96,'S2'!$E$6:$E$23,"Ambos")+SUMIFS('S3'!$I$6:$I$19,'S3'!$B$6:$B$19,$A96,'S3'!$E$6:$E$19,"Víctor")+SUMIFS('S3'!$I$6:$I$19,'S3'!$B$6:$B$19,$A96,'S3'!$E$6:$E$19,"Ambos")+SUMIFS('S4'!$I$6:$I$20,'S4'!$B$6:$B$20,$A96,'S4'!$E$6:$E$20,"Víctor")+SUMIFS('S4'!$I$6:$I$20,'S4'!$B$6:$B$20,$A96,'S4'!$E$6:$E$20,"Ambos")+SUMIFS('S5'!$I$6:$I$20,'S5'!$B$6:$B$20,$A96,'S5'!$E$6:$E$20,"Víctor")+SUMIFS('S5'!$I$6:$I$20,'S5'!$B$6:$B$20,$A96,'S5'!$E$6:$E$20,"Ambos")+SUMIFS('S6'!$I$6:$I$17,'S6'!$B$6:$B$17,$A96,'S6'!$E$6:$E$17,"Víctor")+SUMIFS('S6'!$I$6:$I$17,'S6'!$B$6:$B$17,$A96,'S6'!$E$6:$E$17,"Ambos")+SUMIFS('S7'!$I$6:$I$19,'S7'!$B$6:$B$19,$A96,'S7'!$E$6:$E$19,"Víctor")+SUMIFS('S7'!$I$6:$I$19,'S7'!$B$6:$B$19,$A96,'S7'!$E$6:$E$19,"Ambos")+SUMIFS('S8'!$I$6:$I$23,'S8'!$B$6:$B$23,$A96,'S8'!$E$6:$E$23,"Víctor")+SUMIFS('S8'!$I$6:$I$23,'S8'!$B$6:$B$23,$A96,'S8'!$E$6:$E$23,"Ambos")+SUMIFS('S9'!$I$6:$I$15,'S9'!$B$6:$B$15,$A96,'S9'!$E$6:$E$15,"Víctor")+SUMIFS('S9'!$I$6:$I$15,'S9'!$B$6:$B$15,$A96,'S9'!$E$6:$E$15,"Ambos")+SUMIFS('S10'!$I$6:$I$13,'S10'!$B$6:$B$13,$A96,'S10'!$E$6:$E$13,"Víctor")+SUMIFS('S10'!$I$6:$I$13,'S10'!$B$6:$B$13,$A96,'S10'!$E$6:$E$13,"Ambos")+SUMIFS('Holgura'!$I$6:$I$11,'Holgura'!$B$6:$B$11,$A96,'Holgura'!$E$6:$E$11,"Víctor")+SUMIFS('Holgura'!$I$6:$I$11,'Holgura'!$B$6:$B$11,$A96,'Holgura'!$E$6:$E$11,"Ambos")+SUMIFS('Entrega'!$I$6:$I$9,'Entrega'!$B$6:$B$9,$A96,'Entrega'!$E$6:$E$9,"Víctor")+SUMIFS('Entrega'!$I$6:$I$9,'Entrega'!$B$6:$B$9,$A96,'Entrega'!$E$6:$E$9,"Ambos")+SUMIFS('Defensa'!$I$6:$I$10,'Defensa'!$B$6:$B$10,$A96,'Defensa'!$E$6:$E$10,"Víctor")+SUMIFS('Defensa'!$I$6:$I$10,'Defensa'!$B$6:$B$10,$A96,'Defensa'!$E$6:$E$10,"Ambos")</f>
+        <f>SUMIFS('S1'!$I$6:$I$32,'S1'!$B$6:$B$32,$A96,'S1'!$E$6:$E$32,"Víctor")+SUMIFS('S1'!$I$6:$I$32,'S1'!$B$6:$B$32,$A96,'S1'!$E$6:$E$32,"Ambos")+SUMIFS('S2'!$I$6:$I$23,'S2'!$B$6:$B$23,$A96,'S2'!$E$6:$E$23,"Víctor")+SUMIFS('S2'!$I$6:$I$23,'S2'!$B$6:$B$23,$A96,'S2'!$E$6:$E$23,"Ambos")+SUMIFS('S3'!$I$6:$I$24,'S3'!$B$6:$B$24,$A96,'S3'!$E$6:$E$24,"Víctor")+SUMIFS('S3'!$I$6:$I$24,'S3'!$B$6:$B$24,$A96,'S3'!$E$6:$E$24,"Ambos")+SUMIFS('S4'!$I$6:$I$22,'S4'!$B$6:$B$22,$A96,'S4'!$E$6:$E$22,"Víctor")+SUMIFS('S4'!$I$6:$I$22,'S4'!$B$6:$B$22,$A96,'S4'!$E$6:$E$22,"Ambos")+SUMIFS('S5'!$I$6:$I$20,'S5'!$B$6:$B$20,$A96,'S5'!$E$6:$E$20,"Víctor")+SUMIFS('S5'!$I$6:$I$20,'S5'!$B$6:$B$20,$A96,'S5'!$E$6:$E$20,"Ambos")+SUMIFS('S6'!$I$6:$I$17,'S6'!$B$6:$B$17,$A96,'S6'!$E$6:$E$17,"Víctor")+SUMIFS('S6'!$I$6:$I$17,'S6'!$B$6:$B$17,$A96,'S6'!$E$6:$E$17,"Ambos")+SUMIFS('S7'!$I$6:$I$19,'S7'!$B$6:$B$19,$A96,'S7'!$E$6:$E$19,"Víctor")+SUMIFS('S7'!$I$6:$I$19,'S7'!$B$6:$B$19,$A96,'S7'!$E$6:$E$19,"Ambos")+SUMIFS('S8'!$I$6:$I$23,'S8'!$B$6:$B$23,$A96,'S8'!$E$6:$E$23,"Víctor")+SUMIFS('S8'!$I$6:$I$23,'S8'!$B$6:$B$23,$A96,'S8'!$E$6:$E$23,"Ambos")+SUMIFS('S9'!$I$6:$I$15,'S9'!$B$6:$B$15,$A96,'S9'!$E$6:$E$15,"Víctor")+SUMIFS('S9'!$I$6:$I$15,'S9'!$B$6:$B$15,$A96,'S9'!$E$6:$E$15,"Ambos")+SUMIFS('S10'!$I$6:$I$13,'S10'!$B$6:$B$13,$A96,'S10'!$E$6:$E$13,"Víctor")+SUMIFS('S10'!$I$6:$I$13,'S10'!$B$6:$B$13,$A96,'S10'!$E$6:$E$13,"Ambos")+SUMIFS('Holgura'!$I$6:$I$11,'Holgura'!$B$6:$B$11,$A96,'Holgura'!$E$6:$E$11,"Víctor")+SUMIFS('Holgura'!$I$6:$I$11,'Holgura'!$B$6:$B$11,$A96,'Holgura'!$E$6:$E$11,"Ambos")+SUMIFS('Entrega'!$I$6:$I$9,'Entrega'!$B$6:$B$9,$A96,'Entrega'!$E$6:$E$9,"Víctor")+SUMIFS('Entrega'!$I$6:$I$9,'Entrega'!$B$6:$B$9,$A96,'Entrega'!$E$6:$E$9,"Ambos")+SUMIFS('Defensa'!$I$6:$I$10,'Defensa'!$B$6:$B$10,$A96,'Defensa'!$E$6:$E$10,"Víctor")+SUMIFS('Defensa'!$I$6:$I$10,'Defensa'!$B$6:$B$10,$A96,'Defensa'!$E$6:$E$10,"Ambos")</f>
         <v/>
       </c>
       <c r="E96" s="21">
-        <f>SUMIFS('S1'!$I$6:$I$32,'S1'!$B$6:$B$32,$A96,'S1'!$E$6:$E$32,"Diego")+SUMIFS('S1'!$I$6:$I$32,'S1'!$B$6:$B$32,$A96,'S1'!$E$6:$E$32,"Ambos")+SUMIFS('S2'!$I$6:$I$23,'S2'!$B$6:$B$23,$A96,'S2'!$E$6:$E$23,"Diego")+SUMIFS('S2'!$I$6:$I$23,'S2'!$B$6:$B$23,$A96,'S2'!$E$6:$E$23,"Ambos")+SUMIFS('S3'!$I$6:$I$19,'S3'!$B$6:$B$19,$A96,'S3'!$E$6:$E$19,"Diego")+SUMIFS('S3'!$I$6:$I$19,'S3'!$B$6:$B$19,$A96,'S3'!$E$6:$E$19,"Ambos")+SUMIFS('S4'!$I$6:$I$20,'S4'!$B$6:$B$20,$A96,'S4'!$E$6:$E$20,"Diego")+SUMIFS('S4'!$I$6:$I$20,'S4'!$B$6:$B$20,$A96,'S4'!$E$6:$E$20,"Ambos")+SUMIFS('S5'!$I$6:$I$20,'S5'!$B$6:$B$20,$A96,'S5'!$E$6:$E$20,"Diego")+SUMIFS('S5'!$I$6:$I$20,'S5'!$B$6:$B$20,$A96,'S5'!$E$6:$E$20,"Ambos")+SUMIFS('S6'!$I$6:$I$17,'S6'!$B$6:$B$17,$A96,'S6'!$E$6:$E$17,"Diego")+SUMIFS('S6'!$I$6:$I$17,'S6'!$B$6:$B$17,$A96,'S6'!$E$6:$E$17,"Ambos")+SUMIFS('S7'!$I$6:$I$19,'S7'!$B$6:$B$19,$A96,'S7'!$E$6:$E$19,"Diego")+SUMIFS('S7'!$I$6:$I$19,'S7'!$B$6:$B$19,$A96,'S7'!$E$6:$E$19,"Ambos")+SUMIFS('S8'!$I$6:$I$23,'S8'!$B$6:$B$23,$A96,'S8'!$E$6:$E$23,"Diego")+SUMIFS('S8'!$I$6:$I$23,'S8'!$B$6:$B$23,$A96,'S8'!$E$6:$E$23,"Ambos")+SUMIFS('S9'!$I$6:$I$15,'S9'!$B$6:$B$15,$A96,'S9'!$E$6:$E$15,"Diego")+SUMIFS('S9'!$I$6:$I$15,'S9'!$B$6:$B$15,$A96,'S9'!$E$6:$E$15,"Ambos")+SUMIFS('S10'!$I$6:$I$13,'S10'!$B$6:$B$13,$A96,'S10'!$E$6:$E$13,"Diego")+SUMIFS('S10'!$I$6:$I$13,'S10'!$B$6:$B$13,$A96,'S10'!$E$6:$E$13,"Ambos")+SUMIFS('Holgura'!$I$6:$I$11,'Holgura'!$B$6:$B$11,$A96,'Holgura'!$E$6:$E$11,"Diego")+SUMIFS('Holgura'!$I$6:$I$11,'Holgura'!$B$6:$B$11,$A96,'Holgura'!$E$6:$E$11,"Ambos")+SUMIFS('Entrega'!$I$6:$I$9,'Entrega'!$B$6:$B$9,$A96,'Entrega'!$E$6:$E$9,"Diego")+SUMIFS('Entrega'!$I$6:$I$9,'Entrega'!$B$6:$B$9,$A96,'Entrega'!$E$6:$E$9,"Ambos")+SUMIFS('Defensa'!$I$6:$I$10,'Defensa'!$B$6:$B$10,$A96,'Defensa'!$E$6:$E$10,"Diego")+SUMIFS('Defensa'!$I$6:$I$10,'Defensa'!$B$6:$B$10,$A96,'Defensa'!$E$6:$E$10,"Ambos")</f>
+        <f>SUMIFS('S1'!$I$6:$I$32,'S1'!$B$6:$B$32,$A96,'S1'!$E$6:$E$32,"Diego")+SUMIFS('S1'!$I$6:$I$32,'S1'!$B$6:$B$32,$A96,'S1'!$E$6:$E$32,"Ambos")+SUMIFS('S2'!$I$6:$I$23,'S2'!$B$6:$B$23,$A96,'S2'!$E$6:$E$23,"Diego")+SUMIFS('S2'!$I$6:$I$23,'S2'!$B$6:$B$23,$A96,'S2'!$E$6:$E$23,"Ambos")+SUMIFS('S3'!$I$6:$I$24,'S3'!$B$6:$B$24,$A96,'S3'!$E$6:$E$24,"Diego")+SUMIFS('S3'!$I$6:$I$24,'S3'!$B$6:$B$24,$A96,'S3'!$E$6:$E$24,"Ambos")+SUMIFS('S4'!$I$6:$I$22,'S4'!$B$6:$B$22,$A96,'S4'!$E$6:$E$22,"Diego")+SUMIFS('S4'!$I$6:$I$22,'S4'!$B$6:$B$22,$A96,'S4'!$E$6:$E$22,"Ambos")+SUMIFS('S5'!$I$6:$I$20,'S5'!$B$6:$B$20,$A96,'S5'!$E$6:$E$20,"Diego")+SUMIFS('S5'!$I$6:$I$20,'S5'!$B$6:$B$20,$A96,'S5'!$E$6:$E$20,"Ambos")+SUMIFS('S6'!$I$6:$I$17,'S6'!$B$6:$B$17,$A96,'S6'!$E$6:$E$17,"Diego")+SUMIFS('S6'!$I$6:$I$17,'S6'!$B$6:$B$17,$A96,'S6'!$E$6:$E$17,"Ambos")+SUMIFS('S7'!$I$6:$I$19,'S7'!$B$6:$B$19,$A96,'S7'!$E$6:$E$19,"Diego")+SUMIFS('S7'!$I$6:$I$19,'S7'!$B$6:$B$19,$A96,'S7'!$E$6:$E$19,"Ambos")+SUMIFS('S8'!$I$6:$I$23,'S8'!$B$6:$B$23,$A96,'S8'!$E$6:$E$23,"Diego")+SUMIFS('S8'!$I$6:$I$23,'S8'!$B$6:$B$23,$A96,'S8'!$E$6:$E$23,"Ambos")+SUMIFS('S9'!$I$6:$I$15,'S9'!$B$6:$B$15,$A96,'S9'!$E$6:$E$15,"Diego")+SUMIFS('S9'!$I$6:$I$15,'S9'!$B$6:$B$15,$A96,'S9'!$E$6:$E$15,"Ambos")+SUMIFS('S10'!$I$6:$I$13,'S10'!$B$6:$B$13,$A96,'S10'!$E$6:$E$13,"Diego")+SUMIFS('S10'!$I$6:$I$13,'S10'!$B$6:$B$13,$A96,'S10'!$E$6:$E$13,"Ambos")+SUMIFS('Holgura'!$I$6:$I$11,'Holgura'!$B$6:$B$11,$A96,'Holgura'!$E$6:$E$11,"Diego")+SUMIFS('Holgura'!$I$6:$I$11,'Holgura'!$B$6:$B$11,$A96,'Holgura'!$E$6:$E$11,"Ambos")+SUMIFS('Entrega'!$I$6:$I$9,'Entrega'!$B$6:$B$9,$A96,'Entrega'!$E$6:$E$9,"Diego")+SUMIFS('Entrega'!$I$6:$I$9,'Entrega'!$B$6:$B$9,$A96,'Entrega'!$E$6:$E$9,"Ambos")+SUMIFS('Defensa'!$I$6:$I$10,'Defensa'!$B$6:$B$10,$A96,'Defensa'!$E$6:$E$10,"Diego")+SUMIFS('Defensa'!$I$6:$I$10,'Defensa'!$B$6:$B$10,$A96,'Defensa'!$E$6:$E$10,"Ambos")</f>
         <v/>
       </c>
       <c r="F96" s="21">
-        <f>COUNTIFS('S1'!$B$6:$B$32,$A96,'S1'!$E$6:$E$32,"Víctor")+COUNTIFS('S1'!$B$6:$B$32,$A96,'S1'!$E$6:$E$32,"Ambos")+COUNTIFS('S2'!$B$6:$B$23,$A96,'S2'!$E$6:$E$23,"Víctor")+COUNTIFS('S2'!$B$6:$B$23,$A96,'S2'!$E$6:$E$23,"Ambos")+COUNTIFS('S3'!$B$6:$B$19,$A96,'S3'!$E$6:$E$19,"Víctor")+COUNTIFS('S3'!$B$6:$B$19,$A96,'S3'!$E$6:$E$19,"Ambos")+COUNTIFS('S4'!$B$6:$B$20,$A96,'S4'!$E$6:$E$20,"Víctor")+COUNTIFS('S4'!$B$6:$B$20,$A96,'S4'!$E$6:$E$20,"Ambos")+COUNTIFS('S5'!$B$6:$B$20,$A96,'S5'!$E$6:$E$20,"Víctor")+COUNTIFS('S5'!$B$6:$B$20,$A96,'S5'!$E$6:$E$20,"Ambos")+COUNTIFS('S6'!$B$6:$B$17,$A96,'S6'!$E$6:$E$17,"Víctor")+COUNTIFS('S6'!$B$6:$B$17,$A96,'S6'!$E$6:$E$17,"Ambos")+COUNTIFS('S7'!$B$6:$B$19,$A96,'S7'!$E$6:$E$19,"Víctor")+COUNTIFS('S7'!$B$6:$B$19,$A96,'S7'!$E$6:$E$19,"Ambos")+COUNTIFS('S8'!$B$6:$B$23,$A96,'S8'!$E$6:$E$23,"Víctor")+COUNTIFS('S8'!$B$6:$B$23,$A96,'S8'!$E$6:$E$23,"Ambos")+COUNTIFS('S9'!$B$6:$B$15,$A96,'S9'!$E$6:$E$15,"Víctor")+COUNTIFS('S9'!$B$6:$B$15,$A96,'S9'!$E$6:$E$15,"Ambos")+COUNTIFS('S10'!$B$6:$B$13,$A96,'S10'!$E$6:$E$13,"Víctor")+COUNTIFS('S10'!$B$6:$B$13,$A96,'S10'!$E$6:$E$13,"Ambos")+COUNTIFS('Holgura'!$B$6:$B$11,$A96,'Holgura'!$E$6:$E$11,"Víctor")+COUNTIFS('Holgura'!$B$6:$B$11,$A96,'Holgura'!$E$6:$E$11,"Ambos")+COUNTIFS('Entrega'!$B$6:$B$9,$A96,'Entrega'!$E$6:$E$9,"Víctor")+COUNTIFS('Entrega'!$B$6:$B$9,$A96,'Entrega'!$E$6:$E$9,"Ambos")+COUNTIFS('Defensa'!$B$6:$B$10,$A96,'Defensa'!$E$6:$E$10,"Víctor")+COUNTIFS('Defensa'!$B$6:$B$10,$A96,'Defensa'!$E$6:$E$10,"Ambos")</f>
+        <f>COUNTIFS('S1'!$B$6:$B$32,$A96,'S1'!$E$6:$E$32,"Víctor")+COUNTIFS('S1'!$B$6:$B$32,$A96,'S1'!$E$6:$E$32,"Ambos")+COUNTIFS('S2'!$B$6:$B$23,$A96,'S2'!$E$6:$E$23,"Víctor")+COUNTIFS('S2'!$B$6:$B$23,$A96,'S2'!$E$6:$E$23,"Ambos")+COUNTIFS('S3'!$B$6:$B$24,$A96,'S3'!$E$6:$E$24,"Víctor")+COUNTIFS('S3'!$B$6:$B$24,$A96,'S3'!$E$6:$E$24,"Ambos")+COUNTIFS('S4'!$B$6:$B$22,$A96,'S4'!$E$6:$E$22,"Víctor")+COUNTIFS('S4'!$B$6:$B$22,$A96,'S4'!$E$6:$E$22,"Ambos")+COUNTIFS('S5'!$B$6:$B$20,$A96,'S5'!$E$6:$E$20,"Víctor")+COUNTIFS('S5'!$B$6:$B$20,$A96,'S5'!$E$6:$E$20,"Ambos")+COUNTIFS('S6'!$B$6:$B$17,$A96,'S6'!$E$6:$E$17,"Víctor")+COUNTIFS('S6'!$B$6:$B$17,$A96,'S6'!$E$6:$E$17,"Ambos")+COUNTIFS('S7'!$B$6:$B$19,$A96,'S7'!$E$6:$E$19,"Víctor")+COUNTIFS('S7'!$B$6:$B$19,$A96,'S7'!$E$6:$E$19,"Ambos")+COUNTIFS('S8'!$B$6:$B$23,$A96,'S8'!$E$6:$E$23,"Víctor")+COUNTIFS('S8'!$B$6:$B$23,$A96,'S8'!$E$6:$E$23,"Ambos")+COUNTIFS('S9'!$B$6:$B$15,$A96,'S9'!$E$6:$E$15,"Víctor")+COUNTIFS('S9'!$B$6:$B$15,$A96,'S9'!$E$6:$E$15,"Ambos")+COUNTIFS('S10'!$B$6:$B$13,$A96,'S10'!$E$6:$E$13,"Víctor")+COUNTIFS('S10'!$B$6:$B$13,$A96,'S10'!$E$6:$E$13,"Ambos")+COUNTIFS('Holgura'!$B$6:$B$11,$A96,'Holgura'!$E$6:$E$11,"Víctor")+COUNTIFS('Holgura'!$B$6:$B$11,$A96,'Holgura'!$E$6:$E$11,"Ambos")+COUNTIFS('Entrega'!$B$6:$B$9,$A96,'Entrega'!$E$6:$E$9,"Víctor")+COUNTIFS('Entrega'!$B$6:$B$9,$A96,'Entrega'!$E$6:$E$9,"Ambos")+COUNTIFS('Defensa'!$B$6:$B$10,$A96,'Defensa'!$E$6:$E$10,"Víctor")+COUNTIFS('Defensa'!$B$6:$B$10,$A96,'Defensa'!$E$6:$E$10,"Ambos")</f>
         <v/>
       </c>
       <c r="G96" s="21">
-        <f>COUNTIFS('S1'!$B$6:$B$32,$A96,'S1'!$E$6:$E$32,"Diego")+COUNTIFS('S1'!$B$6:$B$32,$A96,'S1'!$E$6:$E$32,"Ambos")+COUNTIFS('S2'!$B$6:$B$23,$A96,'S2'!$E$6:$E$23,"Diego")+COUNTIFS('S2'!$B$6:$B$23,$A96,'S2'!$E$6:$E$23,"Ambos")+COUNTIFS('S3'!$B$6:$B$19,$A96,'S3'!$E$6:$E$19,"Diego")+COUNTIFS('S3'!$B$6:$B$19,$A96,'S3'!$E$6:$E$19,"Ambos")+COUNTIFS('S4'!$B$6:$B$20,$A96,'S4'!$E$6:$E$20,"Diego")+COUNTIFS('S4'!$B$6:$B$20,$A96,'S4'!$E$6:$E$20,"Ambos")+COUNTIFS('S5'!$B$6:$B$20,$A96,'S5'!$E$6:$E$20,"Diego")+COUNTIFS('S5'!$B$6:$B$20,$A96,'S5'!$E$6:$E$20,"Ambos")+COUNTIFS('S6'!$B$6:$B$17,$A96,'S6'!$E$6:$E$17,"Diego")+COUNTIFS('S6'!$B$6:$B$17,$A96,'S6'!$E$6:$E$17,"Ambos")+COUNTIFS('S7'!$B$6:$B$19,$A96,'S7'!$E$6:$E$19,"Diego")+COUNTIFS('S7'!$B$6:$B$19,$A96,'S7'!$E$6:$E$19,"Ambos")+COUNTIFS('S8'!$B$6:$B$23,$A96,'S8'!$E$6:$E$23,"Diego")+COUNTIFS('S8'!$B$6:$B$23,$A96,'S8'!$E$6:$E$23,"Ambos")+COUNTIFS('S9'!$B$6:$B$15,$A96,'S9'!$E$6:$E$15,"Diego")+COUNTIFS('S9'!$B$6:$B$15,$A96,'S9'!$E$6:$E$15,"Ambos")+COUNTIFS('S10'!$B$6:$B$13,$A96,'S10'!$E$6:$E$13,"Diego")+COUNTIFS('S10'!$B$6:$B$13,$A96,'S10'!$E$6:$E$13,"Ambos")+COUNTIFS('Holgura'!$B$6:$B$11,$A96,'Holgura'!$E$6:$E$11,"Diego")+COUNTIFS('Holgura'!$B$6:$B$11,$A96,'Holgura'!$E$6:$E$11,"Ambos")+COUNTIFS('Entrega'!$B$6:$B$9,$A96,'Entrega'!$E$6:$E$9,"Diego")+COUNTIFS('Entrega'!$B$6:$B$9,$A96,'Entrega'!$E$6:$E$9,"Ambos")+COUNTIFS('Defensa'!$B$6:$B$10,$A96,'Defensa'!$E$6:$E$10,"Diego")+COUNTIFS('Defensa'!$B$6:$B$10,$A96,'Defensa'!$E$6:$E$10,"Ambos")</f>
+        <f>COUNTIFS('S1'!$B$6:$B$32,$A96,'S1'!$E$6:$E$32,"Diego")+COUNTIFS('S1'!$B$6:$B$32,$A96,'S1'!$E$6:$E$32,"Ambos")+COUNTIFS('S2'!$B$6:$B$23,$A96,'S2'!$E$6:$E$23,"Diego")+COUNTIFS('S2'!$B$6:$B$23,$A96,'S2'!$E$6:$E$23,"Ambos")+COUNTIFS('S3'!$B$6:$B$24,$A96,'S3'!$E$6:$E$24,"Diego")+COUNTIFS('S3'!$B$6:$B$24,$A96,'S3'!$E$6:$E$24,"Ambos")+COUNTIFS('S4'!$B$6:$B$22,$A96,'S4'!$E$6:$E$22,"Diego")+COUNTIFS('S4'!$B$6:$B$22,$A96,'S4'!$E$6:$E$22,"Ambos")+COUNTIFS('S5'!$B$6:$B$20,$A96,'S5'!$E$6:$E$20,"Diego")+COUNTIFS('S5'!$B$6:$B$20,$A96,'S5'!$E$6:$E$20,"Ambos")+COUNTIFS('S6'!$B$6:$B$17,$A96,'S6'!$E$6:$E$17,"Diego")+COUNTIFS('S6'!$B$6:$B$17,$A96,'S6'!$E$6:$E$17,"Ambos")+COUNTIFS('S7'!$B$6:$B$19,$A96,'S7'!$E$6:$E$19,"Diego")+COUNTIFS('S7'!$B$6:$B$19,$A96,'S7'!$E$6:$E$19,"Ambos")+COUNTIFS('S8'!$B$6:$B$23,$A96,'S8'!$E$6:$E$23,"Diego")+COUNTIFS('S8'!$B$6:$B$23,$A96,'S8'!$E$6:$E$23,"Ambos")+COUNTIFS('S9'!$B$6:$B$15,$A96,'S9'!$E$6:$E$15,"Diego")+COUNTIFS('S9'!$B$6:$B$15,$A96,'S9'!$E$6:$E$15,"Ambos")+COUNTIFS('S10'!$B$6:$B$13,$A96,'S10'!$E$6:$E$13,"Diego")+COUNTIFS('S10'!$B$6:$B$13,$A96,'S10'!$E$6:$E$13,"Ambos")+COUNTIFS('Holgura'!$B$6:$B$11,$A96,'Holgura'!$E$6:$E$11,"Diego")+COUNTIFS('Holgura'!$B$6:$B$11,$A96,'Holgura'!$E$6:$E$11,"Ambos")+COUNTIFS('Entrega'!$B$6:$B$9,$A96,'Entrega'!$E$6:$E$9,"Diego")+COUNTIFS('Entrega'!$B$6:$B$9,$A96,'Entrega'!$E$6:$E$9,"Ambos")+COUNTIFS('Defensa'!$B$6:$B$10,$A96,'Defensa'!$E$6:$E$10,"Diego")+COUNTIFS('Defensa'!$B$6:$B$10,$A96,'Defensa'!$E$6:$E$10,"Ambos")</f>
         <v/>
       </c>
     </row>
@@ -11348,19 +11369,19 @@
         <v/>
       </c>
       <c r="D97" s="21">
-        <f>SUMIFS('S1'!$I$6:$I$32,'S1'!$B$6:$B$32,$A97,'S1'!$E$6:$E$32,"Víctor")+SUMIFS('S1'!$I$6:$I$32,'S1'!$B$6:$B$32,$A97,'S1'!$E$6:$E$32,"Ambos")+SUMIFS('S2'!$I$6:$I$23,'S2'!$B$6:$B$23,$A97,'S2'!$E$6:$E$23,"Víctor")+SUMIFS('S2'!$I$6:$I$23,'S2'!$B$6:$B$23,$A97,'S2'!$E$6:$E$23,"Ambos")+SUMIFS('S3'!$I$6:$I$19,'S3'!$B$6:$B$19,$A97,'S3'!$E$6:$E$19,"Víctor")+SUMIFS('S3'!$I$6:$I$19,'S3'!$B$6:$B$19,$A97,'S3'!$E$6:$E$19,"Ambos")+SUMIFS('S4'!$I$6:$I$20,'S4'!$B$6:$B$20,$A97,'S4'!$E$6:$E$20,"Víctor")+SUMIFS('S4'!$I$6:$I$20,'S4'!$B$6:$B$20,$A97,'S4'!$E$6:$E$20,"Ambos")+SUMIFS('S5'!$I$6:$I$20,'S5'!$B$6:$B$20,$A97,'S5'!$E$6:$E$20,"Víctor")+SUMIFS('S5'!$I$6:$I$20,'S5'!$B$6:$B$20,$A97,'S5'!$E$6:$E$20,"Ambos")+SUMIFS('S6'!$I$6:$I$17,'S6'!$B$6:$B$17,$A97,'S6'!$E$6:$E$17,"Víctor")+SUMIFS('S6'!$I$6:$I$17,'S6'!$B$6:$B$17,$A97,'S6'!$E$6:$E$17,"Ambos")+SUMIFS('S7'!$I$6:$I$19,'S7'!$B$6:$B$19,$A97,'S7'!$E$6:$E$19,"Víctor")+SUMIFS('S7'!$I$6:$I$19,'S7'!$B$6:$B$19,$A97,'S7'!$E$6:$E$19,"Ambos")+SUMIFS('S8'!$I$6:$I$23,'S8'!$B$6:$B$23,$A97,'S8'!$E$6:$E$23,"Víctor")+SUMIFS('S8'!$I$6:$I$23,'S8'!$B$6:$B$23,$A97,'S8'!$E$6:$E$23,"Ambos")+SUMIFS('S9'!$I$6:$I$15,'S9'!$B$6:$B$15,$A97,'S9'!$E$6:$E$15,"Víctor")+SUMIFS('S9'!$I$6:$I$15,'S9'!$B$6:$B$15,$A97,'S9'!$E$6:$E$15,"Ambos")+SUMIFS('S10'!$I$6:$I$13,'S10'!$B$6:$B$13,$A97,'S10'!$E$6:$E$13,"Víctor")+SUMIFS('S10'!$I$6:$I$13,'S10'!$B$6:$B$13,$A97,'S10'!$E$6:$E$13,"Ambos")+SUMIFS('Holgura'!$I$6:$I$11,'Holgura'!$B$6:$B$11,$A97,'Holgura'!$E$6:$E$11,"Víctor")+SUMIFS('Holgura'!$I$6:$I$11,'Holgura'!$B$6:$B$11,$A97,'Holgura'!$E$6:$E$11,"Ambos")+SUMIFS('Entrega'!$I$6:$I$9,'Entrega'!$B$6:$B$9,$A97,'Entrega'!$E$6:$E$9,"Víctor")+SUMIFS('Entrega'!$I$6:$I$9,'Entrega'!$B$6:$B$9,$A97,'Entrega'!$E$6:$E$9,"Ambos")+SUMIFS('Defensa'!$I$6:$I$10,'Defensa'!$B$6:$B$10,$A97,'Defensa'!$E$6:$E$10,"Víctor")+SUMIFS('Defensa'!$I$6:$I$10,'Defensa'!$B$6:$B$10,$A97,'Defensa'!$E$6:$E$10,"Ambos")</f>
+        <f>SUMIFS('S1'!$I$6:$I$32,'S1'!$B$6:$B$32,$A97,'S1'!$E$6:$E$32,"Víctor")+SUMIFS('S1'!$I$6:$I$32,'S1'!$B$6:$B$32,$A97,'S1'!$E$6:$E$32,"Ambos")+SUMIFS('S2'!$I$6:$I$23,'S2'!$B$6:$B$23,$A97,'S2'!$E$6:$E$23,"Víctor")+SUMIFS('S2'!$I$6:$I$23,'S2'!$B$6:$B$23,$A97,'S2'!$E$6:$E$23,"Ambos")+SUMIFS('S3'!$I$6:$I$24,'S3'!$B$6:$B$24,$A97,'S3'!$E$6:$E$24,"Víctor")+SUMIFS('S3'!$I$6:$I$24,'S3'!$B$6:$B$24,$A97,'S3'!$E$6:$E$24,"Ambos")+SUMIFS('S4'!$I$6:$I$22,'S4'!$B$6:$B$22,$A97,'S4'!$E$6:$E$22,"Víctor")+SUMIFS('S4'!$I$6:$I$22,'S4'!$B$6:$B$22,$A97,'S4'!$E$6:$E$22,"Ambos")+SUMIFS('S5'!$I$6:$I$20,'S5'!$B$6:$B$20,$A97,'S5'!$E$6:$E$20,"Víctor")+SUMIFS('S5'!$I$6:$I$20,'S5'!$B$6:$B$20,$A97,'S5'!$E$6:$E$20,"Ambos")+SUMIFS('S6'!$I$6:$I$17,'S6'!$B$6:$B$17,$A97,'S6'!$E$6:$E$17,"Víctor")+SUMIFS('S6'!$I$6:$I$17,'S6'!$B$6:$B$17,$A97,'S6'!$E$6:$E$17,"Ambos")+SUMIFS('S7'!$I$6:$I$19,'S7'!$B$6:$B$19,$A97,'S7'!$E$6:$E$19,"Víctor")+SUMIFS('S7'!$I$6:$I$19,'S7'!$B$6:$B$19,$A97,'S7'!$E$6:$E$19,"Ambos")+SUMIFS('S8'!$I$6:$I$23,'S8'!$B$6:$B$23,$A97,'S8'!$E$6:$E$23,"Víctor")+SUMIFS('S8'!$I$6:$I$23,'S8'!$B$6:$B$23,$A97,'S8'!$E$6:$E$23,"Ambos")+SUMIFS('S9'!$I$6:$I$15,'S9'!$B$6:$B$15,$A97,'S9'!$E$6:$E$15,"Víctor")+SUMIFS('S9'!$I$6:$I$15,'S9'!$B$6:$B$15,$A97,'S9'!$E$6:$E$15,"Ambos")+SUMIFS('S10'!$I$6:$I$13,'S10'!$B$6:$B$13,$A97,'S10'!$E$6:$E$13,"Víctor")+SUMIFS('S10'!$I$6:$I$13,'S10'!$B$6:$B$13,$A97,'S10'!$E$6:$E$13,"Ambos")+SUMIFS('Holgura'!$I$6:$I$11,'Holgura'!$B$6:$B$11,$A97,'Holgura'!$E$6:$E$11,"Víctor")+SUMIFS('Holgura'!$I$6:$I$11,'Holgura'!$B$6:$B$11,$A97,'Holgura'!$E$6:$E$11,"Ambos")+SUMIFS('Entrega'!$I$6:$I$9,'Entrega'!$B$6:$B$9,$A97,'Entrega'!$E$6:$E$9,"Víctor")+SUMIFS('Entrega'!$I$6:$I$9,'Entrega'!$B$6:$B$9,$A97,'Entrega'!$E$6:$E$9,"Ambos")+SUMIFS('Defensa'!$I$6:$I$10,'Defensa'!$B$6:$B$10,$A97,'Defensa'!$E$6:$E$10,"Víctor")+SUMIFS('Defensa'!$I$6:$I$10,'Defensa'!$B$6:$B$10,$A97,'Defensa'!$E$6:$E$10,"Ambos")</f>
         <v/>
       </c>
       <c r="E97" s="21">
-        <f>SUMIFS('S1'!$I$6:$I$32,'S1'!$B$6:$B$32,$A97,'S1'!$E$6:$E$32,"Diego")+SUMIFS('S1'!$I$6:$I$32,'S1'!$B$6:$B$32,$A97,'S1'!$E$6:$E$32,"Ambos")+SUMIFS('S2'!$I$6:$I$23,'S2'!$B$6:$B$23,$A97,'S2'!$E$6:$E$23,"Diego")+SUMIFS('S2'!$I$6:$I$23,'S2'!$B$6:$B$23,$A97,'S2'!$E$6:$E$23,"Ambos")+SUMIFS('S3'!$I$6:$I$19,'S3'!$B$6:$B$19,$A97,'S3'!$E$6:$E$19,"Diego")+SUMIFS('S3'!$I$6:$I$19,'S3'!$B$6:$B$19,$A97,'S3'!$E$6:$E$19,"Ambos")+SUMIFS('S4'!$I$6:$I$20,'S4'!$B$6:$B$20,$A97,'S4'!$E$6:$E$20,"Diego")+SUMIFS('S4'!$I$6:$I$20,'S4'!$B$6:$B$20,$A97,'S4'!$E$6:$E$20,"Ambos")+SUMIFS('S5'!$I$6:$I$20,'S5'!$B$6:$B$20,$A97,'S5'!$E$6:$E$20,"Diego")+SUMIFS('S5'!$I$6:$I$20,'S5'!$B$6:$B$20,$A97,'S5'!$E$6:$E$20,"Ambos")+SUMIFS('S6'!$I$6:$I$17,'S6'!$B$6:$B$17,$A97,'S6'!$E$6:$E$17,"Diego")+SUMIFS('S6'!$I$6:$I$17,'S6'!$B$6:$B$17,$A97,'S6'!$E$6:$E$17,"Ambos")+SUMIFS('S7'!$I$6:$I$19,'S7'!$B$6:$B$19,$A97,'S7'!$E$6:$E$19,"Diego")+SUMIFS('S7'!$I$6:$I$19,'S7'!$B$6:$B$19,$A97,'S7'!$E$6:$E$19,"Ambos")+SUMIFS('S8'!$I$6:$I$23,'S8'!$B$6:$B$23,$A97,'S8'!$E$6:$E$23,"Diego")+SUMIFS('S8'!$I$6:$I$23,'S8'!$B$6:$B$23,$A97,'S8'!$E$6:$E$23,"Ambos")+SUMIFS('S9'!$I$6:$I$15,'S9'!$B$6:$B$15,$A97,'S9'!$E$6:$E$15,"Diego")+SUMIFS('S9'!$I$6:$I$15,'S9'!$B$6:$B$15,$A97,'S9'!$E$6:$E$15,"Ambos")+SUMIFS('S10'!$I$6:$I$13,'S10'!$B$6:$B$13,$A97,'S10'!$E$6:$E$13,"Diego")+SUMIFS('S10'!$I$6:$I$13,'S10'!$B$6:$B$13,$A97,'S10'!$E$6:$E$13,"Ambos")+SUMIFS('Holgura'!$I$6:$I$11,'Holgura'!$B$6:$B$11,$A97,'Holgura'!$E$6:$E$11,"Diego")+SUMIFS('Holgura'!$I$6:$I$11,'Holgura'!$B$6:$B$11,$A97,'Holgura'!$E$6:$E$11,"Ambos")+SUMIFS('Entrega'!$I$6:$I$9,'Entrega'!$B$6:$B$9,$A97,'Entrega'!$E$6:$E$9,"Diego")+SUMIFS('Entrega'!$I$6:$I$9,'Entrega'!$B$6:$B$9,$A97,'Entrega'!$E$6:$E$9,"Ambos")+SUMIFS('Defensa'!$I$6:$I$10,'Defensa'!$B$6:$B$10,$A97,'Defensa'!$E$6:$E$10,"Diego")+SUMIFS('Defensa'!$I$6:$I$10,'Defensa'!$B$6:$B$10,$A97,'Defensa'!$E$6:$E$10,"Ambos")</f>
+        <f>SUMIFS('S1'!$I$6:$I$32,'S1'!$B$6:$B$32,$A97,'S1'!$E$6:$E$32,"Diego")+SUMIFS('S1'!$I$6:$I$32,'S1'!$B$6:$B$32,$A97,'S1'!$E$6:$E$32,"Ambos")+SUMIFS('S2'!$I$6:$I$23,'S2'!$B$6:$B$23,$A97,'S2'!$E$6:$E$23,"Diego")+SUMIFS('S2'!$I$6:$I$23,'S2'!$B$6:$B$23,$A97,'S2'!$E$6:$E$23,"Ambos")+SUMIFS('S3'!$I$6:$I$24,'S3'!$B$6:$B$24,$A97,'S3'!$E$6:$E$24,"Diego")+SUMIFS('S3'!$I$6:$I$24,'S3'!$B$6:$B$24,$A97,'S3'!$E$6:$E$24,"Ambos")+SUMIFS('S4'!$I$6:$I$22,'S4'!$B$6:$B$22,$A97,'S4'!$E$6:$E$22,"Diego")+SUMIFS('S4'!$I$6:$I$22,'S4'!$B$6:$B$22,$A97,'S4'!$E$6:$E$22,"Ambos")+SUMIFS('S5'!$I$6:$I$20,'S5'!$B$6:$B$20,$A97,'S5'!$E$6:$E$20,"Diego")+SUMIFS('S5'!$I$6:$I$20,'S5'!$B$6:$B$20,$A97,'S5'!$E$6:$E$20,"Ambos")+SUMIFS('S6'!$I$6:$I$17,'S6'!$B$6:$B$17,$A97,'S6'!$E$6:$E$17,"Diego")+SUMIFS('S6'!$I$6:$I$17,'S6'!$B$6:$B$17,$A97,'S6'!$E$6:$E$17,"Ambos")+SUMIFS('S7'!$I$6:$I$19,'S7'!$B$6:$B$19,$A97,'S7'!$E$6:$E$19,"Diego")+SUMIFS('S7'!$I$6:$I$19,'S7'!$B$6:$B$19,$A97,'S7'!$E$6:$E$19,"Ambos")+SUMIFS('S8'!$I$6:$I$23,'S8'!$B$6:$B$23,$A97,'S8'!$E$6:$E$23,"Diego")+SUMIFS('S8'!$I$6:$I$23,'S8'!$B$6:$B$23,$A97,'S8'!$E$6:$E$23,"Ambos")+SUMIFS('S9'!$I$6:$I$15,'S9'!$B$6:$B$15,$A97,'S9'!$E$6:$E$15,"Diego")+SUMIFS('S9'!$I$6:$I$15,'S9'!$B$6:$B$15,$A97,'S9'!$E$6:$E$15,"Ambos")+SUMIFS('S10'!$I$6:$I$13,'S10'!$B$6:$B$13,$A97,'S10'!$E$6:$E$13,"Diego")+SUMIFS('S10'!$I$6:$I$13,'S10'!$B$6:$B$13,$A97,'S10'!$E$6:$E$13,"Ambos")+SUMIFS('Holgura'!$I$6:$I$11,'Holgura'!$B$6:$B$11,$A97,'Holgura'!$E$6:$E$11,"Diego")+SUMIFS('Holgura'!$I$6:$I$11,'Holgura'!$B$6:$B$11,$A97,'Holgura'!$E$6:$E$11,"Ambos")+SUMIFS('Entrega'!$I$6:$I$9,'Entrega'!$B$6:$B$9,$A97,'Entrega'!$E$6:$E$9,"Diego")+SUMIFS('Entrega'!$I$6:$I$9,'Entrega'!$B$6:$B$9,$A97,'Entrega'!$E$6:$E$9,"Ambos")+SUMIFS('Defensa'!$I$6:$I$10,'Defensa'!$B$6:$B$10,$A97,'Defensa'!$E$6:$E$10,"Diego")+SUMIFS('Defensa'!$I$6:$I$10,'Defensa'!$B$6:$B$10,$A97,'Defensa'!$E$6:$E$10,"Ambos")</f>
         <v/>
       </c>
       <c r="F97" s="21">
-        <f>COUNTIFS('S1'!$B$6:$B$32,$A97,'S1'!$E$6:$E$32,"Víctor")+COUNTIFS('S1'!$B$6:$B$32,$A97,'S1'!$E$6:$E$32,"Ambos")+COUNTIFS('S2'!$B$6:$B$23,$A97,'S2'!$E$6:$E$23,"Víctor")+COUNTIFS('S2'!$B$6:$B$23,$A97,'S2'!$E$6:$E$23,"Ambos")+COUNTIFS('S3'!$B$6:$B$19,$A97,'S3'!$E$6:$E$19,"Víctor")+COUNTIFS('S3'!$B$6:$B$19,$A97,'S3'!$E$6:$E$19,"Ambos")+COUNTIFS('S4'!$B$6:$B$20,$A97,'S4'!$E$6:$E$20,"Víctor")+COUNTIFS('S4'!$B$6:$B$20,$A97,'S4'!$E$6:$E$20,"Ambos")+COUNTIFS('S5'!$B$6:$B$20,$A97,'S5'!$E$6:$E$20,"Víctor")+COUNTIFS('S5'!$B$6:$B$20,$A97,'S5'!$E$6:$E$20,"Ambos")+COUNTIFS('S6'!$B$6:$B$17,$A97,'S6'!$E$6:$E$17,"Víctor")+COUNTIFS('S6'!$B$6:$B$17,$A97,'S6'!$E$6:$E$17,"Ambos")+COUNTIFS('S7'!$B$6:$B$19,$A97,'S7'!$E$6:$E$19,"Víctor")+COUNTIFS('S7'!$B$6:$B$19,$A97,'S7'!$E$6:$E$19,"Ambos")+COUNTIFS('S8'!$B$6:$B$23,$A97,'S8'!$E$6:$E$23,"Víctor")+COUNTIFS('S8'!$B$6:$B$23,$A97,'S8'!$E$6:$E$23,"Ambos")+COUNTIFS('S9'!$B$6:$B$15,$A97,'S9'!$E$6:$E$15,"Víctor")+COUNTIFS('S9'!$B$6:$B$15,$A97,'S9'!$E$6:$E$15,"Ambos")+COUNTIFS('S10'!$B$6:$B$13,$A97,'S10'!$E$6:$E$13,"Víctor")+COUNTIFS('S10'!$B$6:$B$13,$A97,'S10'!$E$6:$E$13,"Ambos")+COUNTIFS('Holgura'!$B$6:$B$11,$A97,'Holgura'!$E$6:$E$11,"Víctor")+COUNTIFS('Holgura'!$B$6:$B$11,$A97,'Holgura'!$E$6:$E$11,"Ambos")+COUNTIFS('Entrega'!$B$6:$B$9,$A97,'Entrega'!$E$6:$E$9,"Víctor")+COUNTIFS('Entrega'!$B$6:$B$9,$A97,'Entrega'!$E$6:$E$9,"Ambos")+COUNTIFS('Defensa'!$B$6:$B$10,$A97,'Defensa'!$E$6:$E$10,"Víctor")+COUNTIFS('Defensa'!$B$6:$B$10,$A97,'Defensa'!$E$6:$E$10,"Ambos")</f>
+        <f>COUNTIFS('S1'!$B$6:$B$32,$A97,'S1'!$E$6:$E$32,"Víctor")+COUNTIFS('S1'!$B$6:$B$32,$A97,'S1'!$E$6:$E$32,"Ambos")+COUNTIFS('S2'!$B$6:$B$23,$A97,'S2'!$E$6:$E$23,"Víctor")+COUNTIFS('S2'!$B$6:$B$23,$A97,'S2'!$E$6:$E$23,"Ambos")+COUNTIFS('S3'!$B$6:$B$24,$A97,'S3'!$E$6:$E$24,"Víctor")+COUNTIFS('S3'!$B$6:$B$24,$A97,'S3'!$E$6:$E$24,"Ambos")+COUNTIFS('S4'!$B$6:$B$22,$A97,'S4'!$E$6:$E$22,"Víctor")+COUNTIFS('S4'!$B$6:$B$22,$A97,'S4'!$E$6:$E$22,"Ambos")+COUNTIFS('S5'!$B$6:$B$20,$A97,'S5'!$E$6:$E$20,"Víctor")+COUNTIFS('S5'!$B$6:$B$20,$A97,'S5'!$E$6:$E$20,"Ambos")+COUNTIFS('S6'!$B$6:$B$17,$A97,'S6'!$E$6:$E$17,"Víctor")+COUNTIFS('S6'!$B$6:$B$17,$A97,'S6'!$E$6:$E$17,"Ambos")+COUNTIFS('S7'!$B$6:$B$19,$A97,'S7'!$E$6:$E$19,"Víctor")+COUNTIFS('S7'!$B$6:$B$19,$A97,'S7'!$E$6:$E$19,"Ambos")+COUNTIFS('S8'!$B$6:$B$23,$A97,'S8'!$E$6:$E$23,"Víctor")+COUNTIFS('S8'!$B$6:$B$23,$A97,'S8'!$E$6:$E$23,"Ambos")+COUNTIFS('S9'!$B$6:$B$15,$A97,'S9'!$E$6:$E$15,"Víctor")+COUNTIFS('S9'!$B$6:$B$15,$A97,'S9'!$E$6:$E$15,"Ambos")+COUNTIFS('S10'!$B$6:$B$13,$A97,'S10'!$E$6:$E$13,"Víctor")+COUNTIFS('S10'!$B$6:$B$13,$A97,'S10'!$E$6:$E$13,"Ambos")+COUNTIFS('Holgura'!$B$6:$B$11,$A97,'Holgura'!$E$6:$E$11,"Víctor")+COUNTIFS('Holgura'!$B$6:$B$11,$A97,'Holgura'!$E$6:$E$11,"Ambos")+COUNTIFS('Entrega'!$B$6:$B$9,$A97,'Entrega'!$E$6:$E$9,"Víctor")+COUNTIFS('Entrega'!$B$6:$B$9,$A97,'Entrega'!$E$6:$E$9,"Ambos")+COUNTIFS('Defensa'!$B$6:$B$10,$A97,'Defensa'!$E$6:$E$10,"Víctor")+COUNTIFS('Defensa'!$B$6:$B$10,$A97,'Defensa'!$E$6:$E$10,"Ambos")</f>
         <v/>
       </c>
       <c r="G97" s="21">
-        <f>COUNTIFS('S1'!$B$6:$B$32,$A97,'S1'!$E$6:$E$32,"Diego")+COUNTIFS('S1'!$B$6:$B$32,$A97,'S1'!$E$6:$E$32,"Ambos")+COUNTIFS('S2'!$B$6:$B$23,$A97,'S2'!$E$6:$E$23,"Diego")+COUNTIFS('S2'!$B$6:$B$23,$A97,'S2'!$E$6:$E$23,"Ambos")+COUNTIFS('S3'!$B$6:$B$19,$A97,'S3'!$E$6:$E$19,"Diego")+COUNTIFS('S3'!$B$6:$B$19,$A97,'S3'!$E$6:$E$19,"Ambos")+COUNTIFS('S4'!$B$6:$B$20,$A97,'S4'!$E$6:$E$20,"Diego")+COUNTIFS('S4'!$B$6:$B$20,$A97,'S4'!$E$6:$E$20,"Ambos")+COUNTIFS('S5'!$B$6:$B$20,$A97,'S5'!$E$6:$E$20,"Diego")+COUNTIFS('S5'!$B$6:$B$20,$A97,'S5'!$E$6:$E$20,"Ambos")+COUNTIFS('S6'!$B$6:$B$17,$A97,'S6'!$E$6:$E$17,"Diego")+COUNTIFS('S6'!$B$6:$B$17,$A97,'S6'!$E$6:$E$17,"Ambos")+COUNTIFS('S7'!$B$6:$B$19,$A97,'S7'!$E$6:$E$19,"Diego")+COUNTIFS('S7'!$B$6:$B$19,$A97,'S7'!$E$6:$E$19,"Ambos")+COUNTIFS('S8'!$B$6:$B$23,$A97,'S8'!$E$6:$E$23,"Diego")+COUNTIFS('S8'!$B$6:$B$23,$A97,'S8'!$E$6:$E$23,"Ambos")+COUNTIFS('S9'!$B$6:$B$15,$A97,'S9'!$E$6:$E$15,"Diego")+COUNTIFS('S9'!$B$6:$B$15,$A97,'S9'!$E$6:$E$15,"Ambos")+COUNTIFS('S10'!$B$6:$B$13,$A97,'S10'!$E$6:$E$13,"Diego")+COUNTIFS('S10'!$B$6:$B$13,$A97,'S10'!$E$6:$E$13,"Ambos")+COUNTIFS('Holgura'!$B$6:$B$11,$A97,'Holgura'!$E$6:$E$11,"Diego")+COUNTIFS('Holgura'!$B$6:$B$11,$A97,'Holgura'!$E$6:$E$11,"Ambos")+COUNTIFS('Entrega'!$B$6:$B$9,$A97,'Entrega'!$E$6:$E$9,"Diego")+COUNTIFS('Entrega'!$B$6:$B$9,$A97,'Entrega'!$E$6:$E$9,"Ambos")+COUNTIFS('Defensa'!$B$6:$B$10,$A97,'Defensa'!$E$6:$E$10,"Diego")+COUNTIFS('Defensa'!$B$6:$B$10,$A97,'Defensa'!$E$6:$E$10,"Ambos")</f>
+        <f>COUNTIFS('S1'!$B$6:$B$32,$A97,'S1'!$E$6:$E$32,"Diego")+COUNTIFS('S1'!$B$6:$B$32,$A97,'S1'!$E$6:$E$32,"Ambos")+COUNTIFS('S2'!$B$6:$B$23,$A97,'S2'!$E$6:$E$23,"Diego")+COUNTIFS('S2'!$B$6:$B$23,$A97,'S2'!$E$6:$E$23,"Ambos")+COUNTIFS('S3'!$B$6:$B$24,$A97,'S3'!$E$6:$E$24,"Diego")+COUNTIFS('S3'!$B$6:$B$24,$A97,'S3'!$E$6:$E$24,"Ambos")+COUNTIFS('S4'!$B$6:$B$22,$A97,'S4'!$E$6:$E$22,"Diego")+COUNTIFS('S4'!$B$6:$B$22,$A97,'S4'!$E$6:$E$22,"Ambos")+COUNTIFS('S5'!$B$6:$B$20,$A97,'S5'!$E$6:$E$20,"Diego")+COUNTIFS('S5'!$B$6:$B$20,$A97,'S5'!$E$6:$E$20,"Ambos")+COUNTIFS('S6'!$B$6:$B$17,$A97,'S6'!$E$6:$E$17,"Diego")+COUNTIFS('S6'!$B$6:$B$17,$A97,'S6'!$E$6:$E$17,"Ambos")+COUNTIFS('S7'!$B$6:$B$19,$A97,'S7'!$E$6:$E$19,"Diego")+COUNTIFS('S7'!$B$6:$B$19,$A97,'S7'!$E$6:$E$19,"Ambos")+COUNTIFS('S8'!$B$6:$B$23,$A97,'S8'!$E$6:$E$23,"Diego")+COUNTIFS('S8'!$B$6:$B$23,$A97,'S8'!$E$6:$E$23,"Ambos")+COUNTIFS('S9'!$B$6:$B$15,$A97,'S9'!$E$6:$E$15,"Diego")+COUNTIFS('S9'!$B$6:$B$15,$A97,'S9'!$E$6:$E$15,"Ambos")+COUNTIFS('S10'!$B$6:$B$13,$A97,'S10'!$E$6:$E$13,"Diego")+COUNTIFS('S10'!$B$6:$B$13,$A97,'S10'!$E$6:$E$13,"Ambos")+COUNTIFS('Holgura'!$B$6:$B$11,$A97,'Holgura'!$E$6:$E$11,"Diego")+COUNTIFS('Holgura'!$B$6:$B$11,$A97,'Holgura'!$E$6:$E$11,"Ambos")+COUNTIFS('Entrega'!$B$6:$B$9,$A97,'Entrega'!$E$6:$E$9,"Diego")+COUNTIFS('Entrega'!$B$6:$B$9,$A97,'Entrega'!$E$6:$E$9,"Ambos")+COUNTIFS('Defensa'!$B$6:$B$10,$A97,'Defensa'!$E$6:$E$10,"Diego")+COUNTIFS('Defensa'!$B$6:$B$10,$A97,'Defensa'!$E$6:$E$10,"Ambos")</f>
         <v/>
       </c>
     </row>
@@ -11377,19 +11398,19 @@
         <v/>
       </c>
       <c r="D98" s="21">
-        <f>SUMIFS('S1'!$I$6:$I$32,'S1'!$B$6:$B$32,$A98,'S1'!$E$6:$E$32,"Víctor")+SUMIFS('S1'!$I$6:$I$32,'S1'!$B$6:$B$32,$A98,'S1'!$E$6:$E$32,"Ambos")+SUMIFS('S2'!$I$6:$I$23,'S2'!$B$6:$B$23,$A98,'S2'!$E$6:$E$23,"Víctor")+SUMIFS('S2'!$I$6:$I$23,'S2'!$B$6:$B$23,$A98,'S2'!$E$6:$E$23,"Ambos")+SUMIFS('S3'!$I$6:$I$19,'S3'!$B$6:$B$19,$A98,'S3'!$E$6:$E$19,"Víctor")+SUMIFS('S3'!$I$6:$I$19,'S3'!$B$6:$B$19,$A98,'S3'!$E$6:$E$19,"Ambos")+SUMIFS('S4'!$I$6:$I$20,'S4'!$B$6:$B$20,$A98,'S4'!$E$6:$E$20,"Víctor")+SUMIFS('S4'!$I$6:$I$20,'S4'!$B$6:$B$20,$A98,'S4'!$E$6:$E$20,"Ambos")+SUMIFS('S5'!$I$6:$I$20,'S5'!$B$6:$B$20,$A98,'S5'!$E$6:$E$20,"Víctor")+SUMIFS('S5'!$I$6:$I$20,'S5'!$B$6:$B$20,$A98,'S5'!$E$6:$E$20,"Ambos")+SUMIFS('S6'!$I$6:$I$17,'S6'!$B$6:$B$17,$A98,'S6'!$E$6:$E$17,"Víctor")+SUMIFS('S6'!$I$6:$I$17,'S6'!$B$6:$B$17,$A98,'S6'!$E$6:$E$17,"Ambos")+SUMIFS('S7'!$I$6:$I$19,'S7'!$B$6:$B$19,$A98,'S7'!$E$6:$E$19,"Víctor")+SUMIFS('S7'!$I$6:$I$19,'S7'!$B$6:$B$19,$A98,'S7'!$E$6:$E$19,"Ambos")+SUMIFS('S8'!$I$6:$I$23,'S8'!$B$6:$B$23,$A98,'S8'!$E$6:$E$23,"Víctor")+SUMIFS('S8'!$I$6:$I$23,'S8'!$B$6:$B$23,$A98,'S8'!$E$6:$E$23,"Ambos")+SUMIFS('S9'!$I$6:$I$15,'S9'!$B$6:$B$15,$A98,'S9'!$E$6:$E$15,"Víctor")+SUMIFS('S9'!$I$6:$I$15,'S9'!$B$6:$B$15,$A98,'S9'!$E$6:$E$15,"Ambos")+SUMIFS('S10'!$I$6:$I$13,'S10'!$B$6:$B$13,$A98,'S10'!$E$6:$E$13,"Víctor")+SUMIFS('S10'!$I$6:$I$13,'S10'!$B$6:$B$13,$A98,'S10'!$E$6:$E$13,"Ambos")+SUMIFS('Holgura'!$I$6:$I$11,'Holgura'!$B$6:$B$11,$A98,'Holgura'!$E$6:$E$11,"Víctor")+SUMIFS('Holgura'!$I$6:$I$11,'Holgura'!$B$6:$B$11,$A98,'Holgura'!$E$6:$E$11,"Ambos")+SUMIFS('Entrega'!$I$6:$I$9,'Entrega'!$B$6:$B$9,$A98,'Entrega'!$E$6:$E$9,"Víctor")+SUMIFS('Entrega'!$I$6:$I$9,'Entrega'!$B$6:$B$9,$A98,'Entrega'!$E$6:$E$9,"Ambos")+SUMIFS('Defensa'!$I$6:$I$10,'Defensa'!$B$6:$B$10,$A98,'Defensa'!$E$6:$E$10,"Víctor")+SUMIFS('Defensa'!$I$6:$I$10,'Defensa'!$B$6:$B$10,$A98,'Defensa'!$E$6:$E$10,"Ambos")</f>
+        <f>SUMIFS('S1'!$I$6:$I$32,'S1'!$B$6:$B$32,$A98,'S1'!$E$6:$E$32,"Víctor")+SUMIFS('S1'!$I$6:$I$32,'S1'!$B$6:$B$32,$A98,'S1'!$E$6:$E$32,"Ambos")+SUMIFS('S2'!$I$6:$I$23,'S2'!$B$6:$B$23,$A98,'S2'!$E$6:$E$23,"Víctor")+SUMIFS('S2'!$I$6:$I$23,'S2'!$B$6:$B$23,$A98,'S2'!$E$6:$E$23,"Ambos")+SUMIFS('S3'!$I$6:$I$24,'S3'!$B$6:$B$24,$A98,'S3'!$E$6:$E$24,"Víctor")+SUMIFS('S3'!$I$6:$I$24,'S3'!$B$6:$B$24,$A98,'S3'!$E$6:$E$24,"Ambos")+SUMIFS('S4'!$I$6:$I$22,'S4'!$B$6:$B$22,$A98,'S4'!$E$6:$E$22,"Víctor")+SUMIFS('S4'!$I$6:$I$22,'S4'!$B$6:$B$22,$A98,'S4'!$E$6:$E$22,"Ambos")+SUMIFS('S5'!$I$6:$I$20,'S5'!$B$6:$B$20,$A98,'S5'!$E$6:$E$20,"Víctor")+SUMIFS('S5'!$I$6:$I$20,'S5'!$B$6:$B$20,$A98,'S5'!$E$6:$E$20,"Ambos")+SUMIFS('S6'!$I$6:$I$17,'S6'!$B$6:$B$17,$A98,'S6'!$E$6:$E$17,"Víctor")+SUMIFS('S6'!$I$6:$I$17,'S6'!$B$6:$B$17,$A98,'S6'!$E$6:$E$17,"Ambos")+SUMIFS('S7'!$I$6:$I$19,'S7'!$B$6:$B$19,$A98,'S7'!$E$6:$E$19,"Víctor")+SUMIFS('S7'!$I$6:$I$19,'S7'!$B$6:$B$19,$A98,'S7'!$E$6:$E$19,"Ambos")+SUMIFS('S8'!$I$6:$I$23,'S8'!$B$6:$B$23,$A98,'S8'!$E$6:$E$23,"Víctor")+SUMIFS('S8'!$I$6:$I$23,'S8'!$B$6:$B$23,$A98,'S8'!$E$6:$E$23,"Ambos")+SUMIFS('S9'!$I$6:$I$15,'S9'!$B$6:$B$15,$A98,'S9'!$E$6:$E$15,"Víctor")+SUMIFS('S9'!$I$6:$I$15,'S9'!$B$6:$B$15,$A98,'S9'!$E$6:$E$15,"Ambos")+SUMIFS('S10'!$I$6:$I$13,'S10'!$B$6:$B$13,$A98,'S10'!$E$6:$E$13,"Víctor")+SUMIFS('S10'!$I$6:$I$13,'S10'!$B$6:$B$13,$A98,'S10'!$E$6:$E$13,"Ambos")+SUMIFS('Holgura'!$I$6:$I$11,'Holgura'!$B$6:$B$11,$A98,'Holgura'!$E$6:$E$11,"Víctor")+SUMIFS('Holgura'!$I$6:$I$11,'Holgura'!$B$6:$B$11,$A98,'Holgura'!$E$6:$E$11,"Ambos")+SUMIFS('Entrega'!$I$6:$I$9,'Entrega'!$B$6:$B$9,$A98,'Entrega'!$E$6:$E$9,"Víctor")+SUMIFS('Entrega'!$I$6:$I$9,'Entrega'!$B$6:$B$9,$A98,'Entrega'!$E$6:$E$9,"Ambos")+SUMIFS('Defensa'!$I$6:$I$10,'Defensa'!$B$6:$B$10,$A98,'Defensa'!$E$6:$E$10,"Víctor")+SUMIFS('Defensa'!$I$6:$I$10,'Defensa'!$B$6:$B$10,$A98,'Defensa'!$E$6:$E$10,"Ambos")</f>
         <v/>
       </c>
       <c r="E98" s="21">
-        <f>SUMIFS('S1'!$I$6:$I$32,'S1'!$B$6:$B$32,$A98,'S1'!$E$6:$E$32,"Diego")+SUMIFS('S1'!$I$6:$I$32,'S1'!$B$6:$B$32,$A98,'S1'!$E$6:$E$32,"Ambos")+SUMIFS('S2'!$I$6:$I$23,'S2'!$B$6:$B$23,$A98,'S2'!$E$6:$E$23,"Diego")+SUMIFS('S2'!$I$6:$I$23,'S2'!$B$6:$B$23,$A98,'S2'!$E$6:$E$23,"Ambos")+SUMIFS('S3'!$I$6:$I$19,'S3'!$B$6:$B$19,$A98,'S3'!$E$6:$E$19,"Diego")+SUMIFS('S3'!$I$6:$I$19,'S3'!$B$6:$B$19,$A98,'S3'!$E$6:$E$19,"Ambos")+SUMIFS('S4'!$I$6:$I$20,'S4'!$B$6:$B$20,$A98,'S4'!$E$6:$E$20,"Diego")+SUMIFS('S4'!$I$6:$I$20,'S4'!$B$6:$B$20,$A98,'S4'!$E$6:$E$20,"Ambos")+SUMIFS('S5'!$I$6:$I$20,'S5'!$B$6:$B$20,$A98,'S5'!$E$6:$E$20,"Diego")+SUMIFS('S5'!$I$6:$I$20,'S5'!$B$6:$B$20,$A98,'S5'!$E$6:$E$20,"Ambos")+SUMIFS('S6'!$I$6:$I$17,'S6'!$B$6:$B$17,$A98,'S6'!$E$6:$E$17,"Diego")+SUMIFS('S6'!$I$6:$I$17,'S6'!$B$6:$B$17,$A98,'S6'!$E$6:$E$17,"Ambos")+SUMIFS('S7'!$I$6:$I$19,'S7'!$B$6:$B$19,$A98,'S7'!$E$6:$E$19,"Diego")+SUMIFS('S7'!$I$6:$I$19,'S7'!$B$6:$B$19,$A98,'S7'!$E$6:$E$19,"Ambos")+SUMIFS('S8'!$I$6:$I$23,'S8'!$B$6:$B$23,$A98,'S8'!$E$6:$E$23,"Diego")+SUMIFS('S8'!$I$6:$I$23,'S8'!$B$6:$B$23,$A98,'S8'!$E$6:$E$23,"Ambos")+SUMIFS('S9'!$I$6:$I$15,'S9'!$B$6:$B$15,$A98,'S9'!$E$6:$E$15,"Diego")+SUMIFS('S9'!$I$6:$I$15,'S9'!$B$6:$B$15,$A98,'S9'!$E$6:$E$15,"Ambos")+SUMIFS('S10'!$I$6:$I$13,'S10'!$B$6:$B$13,$A98,'S10'!$E$6:$E$13,"Diego")+SUMIFS('S10'!$I$6:$I$13,'S10'!$B$6:$B$13,$A98,'S10'!$E$6:$E$13,"Ambos")+SUMIFS('Holgura'!$I$6:$I$11,'Holgura'!$B$6:$B$11,$A98,'Holgura'!$E$6:$E$11,"Diego")+SUMIFS('Holgura'!$I$6:$I$11,'Holgura'!$B$6:$B$11,$A98,'Holgura'!$E$6:$E$11,"Ambos")+SUMIFS('Entrega'!$I$6:$I$9,'Entrega'!$B$6:$B$9,$A98,'Entrega'!$E$6:$E$9,"Diego")+SUMIFS('Entrega'!$I$6:$I$9,'Entrega'!$B$6:$B$9,$A98,'Entrega'!$E$6:$E$9,"Ambos")+SUMIFS('Defensa'!$I$6:$I$10,'Defensa'!$B$6:$B$10,$A98,'Defensa'!$E$6:$E$10,"Diego")+SUMIFS('Defensa'!$I$6:$I$10,'Defensa'!$B$6:$B$10,$A98,'Defensa'!$E$6:$E$10,"Ambos")</f>
+        <f>SUMIFS('S1'!$I$6:$I$32,'S1'!$B$6:$B$32,$A98,'S1'!$E$6:$E$32,"Diego")+SUMIFS('S1'!$I$6:$I$32,'S1'!$B$6:$B$32,$A98,'S1'!$E$6:$E$32,"Ambos")+SUMIFS('S2'!$I$6:$I$23,'S2'!$B$6:$B$23,$A98,'S2'!$E$6:$E$23,"Diego")+SUMIFS('S2'!$I$6:$I$23,'S2'!$B$6:$B$23,$A98,'S2'!$E$6:$E$23,"Ambos")+SUMIFS('S3'!$I$6:$I$24,'S3'!$B$6:$B$24,$A98,'S3'!$E$6:$E$24,"Diego")+SUMIFS('S3'!$I$6:$I$24,'S3'!$B$6:$B$24,$A98,'S3'!$E$6:$E$24,"Ambos")+SUMIFS('S4'!$I$6:$I$22,'S4'!$B$6:$B$22,$A98,'S4'!$E$6:$E$22,"Diego")+SUMIFS('S4'!$I$6:$I$22,'S4'!$B$6:$B$22,$A98,'S4'!$E$6:$E$22,"Ambos")+SUMIFS('S5'!$I$6:$I$20,'S5'!$B$6:$B$20,$A98,'S5'!$E$6:$E$20,"Diego")+SUMIFS('S5'!$I$6:$I$20,'S5'!$B$6:$B$20,$A98,'S5'!$E$6:$E$20,"Ambos")+SUMIFS('S6'!$I$6:$I$17,'S6'!$B$6:$B$17,$A98,'S6'!$E$6:$E$17,"Diego")+SUMIFS('S6'!$I$6:$I$17,'S6'!$B$6:$B$17,$A98,'S6'!$E$6:$E$17,"Ambos")+SUMIFS('S7'!$I$6:$I$19,'S7'!$B$6:$B$19,$A98,'S7'!$E$6:$E$19,"Diego")+SUMIFS('S7'!$I$6:$I$19,'S7'!$B$6:$B$19,$A98,'S7'!$E$6:$E$19,"Ambos")+SUMIFS('S8'!$I$6:$I$23,'S8'!$B$6:$B$23,$A98,'S8'!$E$6:$E$23,"Diego")+SUMIFS('S8'!$I$6:$I$23,'S8'!$B$6:$B$23,$A98,'S8'!$E$6:$E$23,"Ambos")+SUMIFS('S9'!$I$6:$I$15,'S9'!$B$6:$B$15,$A98,'S9'!$E$6:$E$15,"Diego")+SUMIFS('S9'!$I$6:$I$15,'S9'!$B$6:$B$15,$A98,'S9'!$E$6:$E$15,"Ambos")+SUMIFS('S10'!$I$6:$I$13,'S10'!$B$6:$B$13,$A98,'S10'!$E$6:$E$13,"Diego")+SUMIFS('S10'!$I$6:$I$13,'S10'!$B$6:$B$13,$A98,'S10'!$E$6:$E$13,"Ambos")+SUMIFS('Holgura'!$I$6:$I$11,'Holgura'!$B$6:$B$11,$A98,'Holgura'!$E$6:$E$11,"Diego")+SUMIFS('Holgura'!$I$6:$I$11,'Holgura'!$B$6:$B$11,$A98,'Holgura'!$E$6:$E$11,"Ambos")+SUMIFS('Entrega'!$I$6:$I$9,'Entrega'!$B$6:$B$9,$A98,'Entrega'!$E$6:$E$9,"Diego")+SUMIFS('Entrega'!$I$6:$I$9,'Entrega'!$B$6:$B$9,$A98,'Entrega'!$E$6:$E$9,"Ambos")+SUMIFS('Defensa'!$I$6:$I$10,'Defensa'!$B$6:$B$10,$A98,'Defensa'!$E$6:$E$10,"Diego")+SUMIFS('Defensa'!$I$6:$I$10,'Defensa'!$B$6:$B$10,$A98,'Defensa'!$E$6:$E$10,"Ambos")</f>
         <v/>
       </c>
       <c r="F98" s="21">
-        <f>COUNTIFS('S1'!$B$6:$B$32,$A98,'S1'!$E$6:$E$32,"Víctor")+COUNTIFS('S1'!$B$6:$B$32,$A98,'S1'!$E$6:$E$32,"Ambos")+COUNTIFS('S2'!$B$6:$B$23,$A98,'S2'!$E$6:$E$23,"Víctor")+COUNTIFS('S2'!$B$6:$B$23,$A98,'S2'!$E$6:$E$23,"Ambos")+COUNTIFS('S3'!$B$6:$B$19,$A98,'S3'!$E$6:$E$19,"Víctor")+COUNTIFS('S3'!$B$6:$B$19,$A98,'S3'!$E$6:$E$19,"Ambos")+COUNTIFS('S4'!$B$6:$B$20,$A98,'S4'!$E$6:$E$20,"Víctor")+COUNTIFS('S4'!$B$6:$B$20,$A98,'S4'!$E$6:$E$20,"Ambos")+COUNTIFS('S5'!$B$6:$B$20,$A98,'S5'!$E$6:$E$20,"Víctor")+COUNTIFS('S5'!$B$6:$B$20,$A98,'S5'!$E$6:$E$20,"Ambos")+COUNTIFS('S6'!$B$6:$B$17,$A98,'S6'!$E$6:$E$17,"Víctor")+COUNTIFS('S6'!$B$6:$B$17,$A98,'S6'!$E$6:$E$17,"Ambos")+COUNTIFS('S7'!$B$6:$B$19,$A98,'S7'!$E$6:$E$19,"Víctor")+COUNTIFS('S7'!$B$6:$B$19,$A98,'S7'!$E$6:$E$19,"Ambos")+COUNTIFS('S8'!$B$6:$B$23,$A98,'S8'!$E$6:$E$23,"Víctor")+COUNTIFS('S8'!$B$6:$B$23,$A98,'S8'!$E$6:$E$23,"Ambos")+COUNTIFS('S9'!$B$6:$B$15,$A98,'S9'!$E$6:$E$15,"Víctor")+COUNTIFS('S9'!$B$6:$B$15,$A98,'S9'!$E$6:$E$15,"Ambos")+COUNTIFS('S10'!$B$6:$B$13,$A98,'S10'!$E$6:$E$13,"Víctor")+COUNTIFS('S10'!$B$6:$B$13,$A98,'S10'!$E$6:$E$13,"Ambos")+COUNTIFS('Holgura'!$B$6:$B$11,$A98,'Holgura'!$E$6:$E$11,"Víctor")+COUNTIFS('Holgura'!$B$6:$B$11,$A98,'Holgura'!$E$6:$E$11,"Ambos")+COUNTIFS('Entrega'!$B$6:$B$9,$A98,'Entrega'!$E$6:$E$9,"Víctor")+COUNTIFS('Entrega'!$B$6:$B$9,$A98,'Entrega'!$E$6:$E$9,"Ambos")+COUNTIFS('Defensa'!$B$6:$B$10,$A98,'Defensa'!$E$6:$E$10,"Víctor")+COUNTIFS('Defensa'!$B$6:$B$10,$A98,'Defensa'!$E$6:$E$10,"Ambos")</f>
+        <f>COUNTIFS('S1'!$B$6:$B$32,$A98,'S1'!$E$6:$E$32,"Víctor")+COUNTIFS('S1'!$B$6:$B$32,$A98,'S1'!$E$6:$E$32,"Ambos")+COUNTIFS('S2'!$B$6:$B$23,$A98,'S2'!$E$6:$E$23,"Víctor")+COUNTIFS('S2'!$B$6:$B$23,$A98,'S2'!$E$6:$E$23,"Ambos")+COUNTIFS('S3'!$B$6:$B$24,$A98,'S3'!$E$6:$E$24,"Víctor")+COUNTIFS('S3'!$B$6:$B$24,$A98,'S3'!$E$6:$E$24,"Ambos")+COUNTIFS('S4'!$B$6:$B$22,$A98,'S4'!$E$6:$E$22,"Víctor")+COUNTIFS('S4'!$B$6:$B$22,$A98,'S4'!$E$6:$E$22,"Ambos")+COUNTIFS('S5'!$B$6:$B$20,$A98,'S5'!$E$6:$E$20,"Víctor")+COUNTIFS('S5'!$B$6:$B$20,$A98,'S5'!$E$6:$E$20,"Ambos")+COUNTIFS('S6'!$B$6:$B$17,$A98,'S6'!$E$6:$E$17,"Víctor")+COUNTIFS('S6'!$B$6:$B$17,$A98,'S6'!$E$6:$E$17,"Ambos")+COUNTIFS('S7'!$B$6:$B$19,$A98,'S7'!$E$6:$E$19,"Víctor")+COUNTIFS('S7'!$B$6:$B$19,$A98,'S7'!$E$6:$E$19,"Ambos")+COUNTIFS('S8'!$B$6:$B$23,$A98,'S8'!$E$6:$E$23,"Víctor")+COUNTIFS('S8'!$B$6:$B$23,$A98,'S8'!$E$6:$E$23,"Ambos")+COUNTIFS('S9'!$B$6:$B$15,$A98,'S9'!$E$6:$E$15,"Víctor")+COUNTIFS('S9'!$B$6:$B$15,$A98,'S9'!$E$6:$E$15,"Ambos")+COUNTIFS('S10'!$B$6:$B$13,$A98,'S10'!$E$6:$E$13,"Víctor")+COUNTIFS('S10'!$B$6:$B$13,$A98,'S10'!$E$6:$E$13,"Ambos")+COUNTIFS('Holgura'!$B$6:$B$11,$A98,'Holgura'!$E$6:$E$11,"Víctor")+COUNTIFS('Holgura'!$B$6:$B$11,$A98,'Holgura'!$E$6:$E$11,"Ambos")+COUNTIFS('Entrega'!$B$6:$B$9,$A98,'Entrega'!$E$6:$E$9,"Víctor")+COUNTIFS('Entrega'!$B$6:$B$9,$A98,'Entrega'!$E$6:$E$9,"Ambos")+COUNTIFS('Defensa'!$B$6:$B$10,$A98,'Defensa'!$E$6:$E$10,"Víctor")+COUNTIFS('Defensa'!$B$6:$B$10,$A98,'Defensa'!$E$6:$E$10,"Ambos")</f>
         <v/>
       </c>
       <c r="G98" s="21">
-        <f>COUNTIFS('S1'!$B$6:$B$32,$A98,'S1'!$E$6:$E$32,"Diego")+COUNTIFS('S1'!$B$6:$B$32,$A98,'S1'!$E$6:$E$32,"Ambos")+COUNTIFS('S2'!$B$6:$B$23,$A98,'S2'!$E$6:$E$23,"Diego")+COUNTIFS('S2'!$B$6:$B$23,$A98,'S2'!$E$6:$E$23,"Ambos")+COUNTIFS('S3'!$B$6:$B$19,$A98,'S3'!$E$6:$E$19,"Diego")+COUNTIFS('S3'!$B$6:$B$19,$A98,'S3'!$E$6:$E$19,"Ambos")+COUNTIFS('S4'!$B$6:$B$20,$A98,'S4'!$E$6:$E$20,"Diego")+COUNTIFS('S4'!$B$6:$B$20,$A98,'S4'!$E$6:$E$20,"Ambos")+COUNTIFS('S5'!$B$6:$B$20,$A98,'S5'!$E$6:$E$20,"Diego")+COUNTIFS('S5'!$B$6:$B$20,$A98,'S5'!$E$6:$E$20,"Ambos")+COUNTIFS('S6'!$B$6:$B$17,$A98,'S6'!$E$6:$E$17,"Diego")+COUNTIFS('S6'!$B$6:$B$17,$A98,'S6'!$E$6:$E$17,"Ambos")+COUNTIFS('S7'!$B$6:$B$19,$A98,'S7'!$E$6:$E$19,"Diego")+COUNTIFS('S7'!$B$6:$B$19,$A98,'S7'!$E$6:$E$19,"Ambos")+COUNTIFS('S8'!$B$6:$B$23,$A98,'S8'!$E$6:$E$23,"Diego")+COUNTIFS('S8'!$B$6:$B$23,$A98,'S8'!$E$6:$E$23,"Ambos")+COUNTIFS('S9'!$B$6:$B$15,$A98,'S9'!$E$6:$E$15,"Diego")+COUNTIFS('S9'!$B$6:$B$15,$A98,'S9'!$E$6:$E$15,"Ambos")+COUNTIFS('S10'!$B$6:$B$13,$A98,'S10'!$E$6:$E$13,"Diego")+COUNTIFS('S10'!$B$6:$B$13,$A98,'S10'!$E$6:$E$13,"Ambos")+COUNTIFS('Holgura'!$B$6:$B$11,$A98,'Holgura'!$E$6:$E$11,"Diego")+COUNTIFS('Holgura'!$B$6:$B$11,$A98,'Holgura'!$E$6:$E$11,"Ambos")+COUNTIFS('Entrega'!$B$6:$B$9,$A98,'Entrega'!$E$6:$E$9,"Diego")+COUNTIFS('Entrega'!$B$6:$B$9,$A98,'Entrega'!$E$6:$E$9,"Ambos")+COUNTIFS('Defensa'!$B$6:$B$10,$A98,'Defensa'!$E$6:$E$10,"Diego")+COUNTIFS('Defensa'!$B$6:$B$10,$A98,'Defensa'!$E$6:$E$10,"Ambos")</f>
+        <f>COUNTIFS('S1'!$B$6:$B$32,$A98,'S1'!$E$6:$E$32,"Diego")+COUNTIFS('S1'!$B$6:$B$32,$A98,'S1'!$E$6:$E$32,"Ambos")+COUNTIFS('S2'!$B$6:$B$23,$A98,'S2'!$E$6:$E$23,"Diego")+COUNTIFS('S2'!$B$6:$B$23,$A98,'S2'!$E$6:$E$23,"Ambos")+COUNTIFS('S3'!$B$6:$B$24,$A98,'S3'!$E$6:$E$24,"Diego")+COUNTIFS('S3'!$B$6:$B$24,$A98,'S3'!$E$6:$E$24,"Ambos")+COUNTIFS('S4'!$B$6:$B$22,$A98,'S4'!$E$6:$E$22,"Diego")+COUNTIFS('S4'!$B$6:$B$22,$A98,'S4'!$E$6:$E$22,"Ambos")+COUNTIFS('S5'!$B$6:$B$20,$A98,'S5'!$E$6:$E$20,"Diego")+COUNTIFS('S5'!$B$6:$B$20,$A98,'S5'!$E$6:$E$20,"Ambos")+COUNTIFS('S6'!$B$6:$B$17,$A98,'S6'!$E$6:$E$17,"Diego")+COUNTIFS('S6'!$B$6:$B$17,$A98,'S6'!$E$6:$E$17,"Ambos")+COUNTIFS('S7'!$B$6:$B$19,$A98,'S7'!$E$6:$E$19,"Diego")+COUNTIFS('S7'!$B$6:$B$19,$A98,'S7'!$E$6:$E$19,"Ambos")+COUNTIFS('S8'!$B$6:$B$23,$A98,'S8'!$E$6:$E$23,"Diego")+COUNTIFS('S8'!$B$6:$B$23,$A98,'S8'!$E$6:$E$23,"Ambos")+COUNTIFS('S9'!$B$6:$B$15,$A98,'S9'!$E$6:$E$15,"Diego")+COUNTIFS('S9'!$B$6:$B$15,$A98,'S9'!$E$6:$E$15,"Ambos")+COUNTIFS('S10'!$B$6:$B$13,$A98,'S10'!$E$6:$E$13,"Diego")+COUNTIFS('S10'!$B$6:$B$13,$A98,'S10'!$E$6:$E$13,"Ambos")+COUNTIFS('Holgura'!$B$6:$B$11,$A98,'Holgura'!$E$6:$E$11,"Diego")+COUNTIFS('Holgura'!$B$6:$B$11,$A98,'Holgura'!$E$6:$E$11,"Ambos")+COUNTIFS('Entrega'!$B$6:$B$9,$A98,'Entrega'!$E$6:$E$9,"Diego")+COUNTIFS('Entrega'!$B$6:$B$9,$A98,'Entrega'!$E$6:$E$9,"Ambos")+COUNTIFS('Defensa'!$B$6:$B$10,$A98,'Defensa'!$E$6:$E$10,"Diego")+COUNTIFS('Defensa'!$B$6:$B$10,$A98,'Defensa'!$E$6:$E$10,"Ambos")</f>
         <v/>
       </c>
     </row>
@@ -11406,19 +11427,19 @@
         <v/>
       </c>
       <c r="D99" s="21">
-        <f>SUMIFS('S1'!$I$6:$I$32,'S1'!$B$6:$B$32,$A99,'S1'!$E$6:$E$32,"Víctor")+SUMIFS('S1'!$I$6:$I$32,'S1'!$B$6:$B$32,$A99,'S1'!$E$6:$E$32,"Ambos")+SUMIFS('S2'!$I$6:$I$23,'S2'!$B$6:$B$23,$A99,'S2'!$E$6:$E$23,"Víctor")+SUMIFS('S2'!$I$6:$I$23,'S2'!$B$6:$B$23,$A99,'S2'!$E$6:$E$23,"Ambos")+SUMIFS('S3'!$I$6:$I$19,'S3'!$B$6:$B$19,$A99,'S3'!$E$6:$E$19,"Víctor")+SUMIFS('S3'!$I$6:$I$19,'S3'!$B$6:$B$19,$A99,'S3'!$E$6:$E$19,"Ambos")+SUMIFS('S4'!$I$6:$I$20,'S4'!$B$6:$B$20,$A99,'S4'!$E$6:$E$20,"Víctor")+SUMIFS('S4'!$I$6:$I$20,'S4'!$B$6:$B$20,$A99,'S4'!$E$6:$E$20,"Ambos")+SUMIFS('S5'!$I$6:$I$20,'S5'!$B$6:$B$20,$A99,'S5'!$E$6:$E$20,"Víctor")+SUMIFS('S5'!$I$6:$I$20,'S5'!$B$6:$B$20,$A99,'S5'!$E$6:$E$20,"Ambos")+SUMIFS('S6'!$I$6:$I$17,'S6'!$B$6:$B$17,$A99,'S6'!$E$6:$E$17,"Víctor")+SUMIFS('S6'!$I$6:$I$17,'S6'!$B$6:$B$17,$A99,'S6'!$E$6:$E$17,"Ambos")+SUMIFS('S7'!$I$6:$I$19,'S7'!$B$6:$B$19,$A99,'S7'!$E$6:$E$19,"Víctor")+SUMIFS('S7'!$I$6:$I$19,'S7'!$B$6:$B$19,$A99,'S7'!$E$6:$E$19,"Ambos")+SUMIFS('S8'!$I$6:$I$23,'S8'!$B$6:$B$23,$A99,'S8'!$E$6:$E$23,"Víctor")+SUMIFS('S8'!$I$6:$I$23,'S8'!$B$6:$B$23,$A99,'S8'!$E$6:$E$23,"Ambos")+SUMIFS('S9'!$I$6:$I$15,'S9'!$B$6:$B$15,$A99,'S9'!$E$6:$E$15,"Víctor")+SUMIFS('S9'!$I$6:$I$15,'S9'!$B$6:$B$15,$A99,'S9'!$E$6:$E$15,"Ambos")+SUMIFS('S10'!$I$6:$I$13,'S10'!$B$6:$B$13,$A99,'S10'!$E$6:$E$13,"Víctor")+SUMIFS('S10'!$I$6:$I$13,'S10'!$B$6:$B$13,$A99,'S10'!$E$6:$E$13,"Ambos")+SUMIFS('Holgura'!$I$6:$I$11,'Holgura'!$B$6:$B$11,$A99,'Holgura'!$E$6:$E$11,"Víctor")+SUMIFS('Holgura'!$I$6:$I$11,'Holgura'!$B$6:$B$11,$A99,'Holgura'!$E$6:$E$11,"Ambos")+SUMIFS('Entrega'!$I$6:$I$9,'Entrega'!$B$6:$B$9,$A99,'Entrega'!$E$6:$E$9,"Víctor")+SUMIFS('Entrega'!$I$6:$I$9,'Entrega'!$B$6:$B$9,$A99,'Entrega'!$E$6:$E$9,"Ambos")+SUMIFS('Defensa'!$I$6:$I$10,'Defensa'!$B$6:$B$10,$A99,'Defensa'!$E$6:$E$10,"Víctor")+SUMIFS('Defensa'!$I$6:$I$10,'Defensa'!$B$6:$B$10,$A99,'Defensa'!$E$6:$E$10,"Ambos")</f>
+        <f>SUMIFS('S1'!$I$6:$I$32,'S1'!$B$6:$B$32,$A99,'S1'!$E$6:$E$32,"Víctor")+SUMIFS('S1'!$I$6:$I$32,'S1'!$B$6:$B$32,$A99,'S1'!$E$6:$E$32,"Ambos")+SUMIFS('S2'!$I$6:$I$23,'S2'!$B$6:$B$23,$A99,'S2'!$E$6:$E$23,"Víctor")+SUMIFS('S2'!$I$6:$I$23,'S2'!$B$6:$B$23,$A99,'S2'!$E$6:$E$23,"Ambos")+SUMIFS('S3'!$I$6:$I$24,'S3'!$B$6:$B$24,$A99,'S3'!$E$6:$E$24,"Víctor")+SUMIFS('S3'!$I$6:$I$24,'S3'!$B$6:$B$24,$A99,'S3'!$E$6:$E$24,"Ambos")+SUMIFS('S4'!$I$6:$I$22,'S4'!$B$6:$B$22,$A99,'S4'!$E$6:$E$22,"Víctor")+SUMIFS('S4'!$I$6:$I$22,'S4'!$B$6:$B$22,$A99,'S4'!$E$6:$E$22,"Ambos")+SUMIFS('S5'!$I$6:$I$20,'S5'!$B$6:$B$20,$A99,'S5'!$E$6:$E$20,"Víctor")+SUMIFS('S5'!$I$6:$I$20,'S5'!$B$6:$B$20,$A99,'S5'!$E$6:$E$20,"Ambos")+SUMIFS('S6'!$I$6:$I$17,'S6'!$B$6:$B$17,$A99,'S6'!$E$6:$E$17,"Víctor")+SUMIFS('S6'!$I$6:$I$17,'S6'!$B$6:$B$17,$A99,'S6'!$E$6:$E$17,"Ambos")+SUMIFS('S7'!$I$6:$I$19,'S7'!$B$6:$B$19,$A99,'S7'!$E$6:$E$19,"Víctor")+SUMIFS('S7'!$I$6:$I$19,'S7'!$B$6:$B$19,$A99,'S7'!$E$6:$E$19,"Ambos")+SUMIFS('S8'!$I$6:$I$23,'S8'!$B$6:$B$23,$A99,'S8'!$E$6:$E$23,"Víctor")+SUMIFS('S8'!$I$6:$I$23,'S8'!$B$6:$B$23,$A99,'S8'!$E$6:$E$23,"Ambos")+SUMIFS('S9'!$I$6:$I$15,'S9'!$B$6:$B$15,$A99,'S9'!$E$6:$E$15,"Víctor")+SUMIFS('S9'!$I$6:$I$15,'S9'!$B$6:$B$15,$A99,'S9'!$E$6:$E$15,"Ambos")+SUMIFS('S10'!$I$6:$I$13,'S10'!$B$6:$B$13,$A99,'S10'!$E$6:$E$13,"Víctor")+SUMIFS('S10'!$I$6:$I$13,'S10'!$B$6:$B$13,$A99,'S10'!$E$6:$E$13,"Ambos")+SUMIFS('Holgura'!$I$6:$I$11,'Holgura'!$B$6:$B$11,$A99,'Holgura'!$E$6:$E$11,"Víctor")+SUMIFS('Holgura'!$I$6:$I$11,'Holgura'!$B$6:$B$11,$A99,'Holgura'!$E$6:$E$11,"Ambos")+SUMIFS('Entrega'!$I$6:$I$9,'Entrega'!$B$6:$B$9,$A99,'Entrega'!$E$6:$E$9,"Víctor")+SUMIFS('Entrega'!$I$6:$I$9,'Entrega'!$B$6:$B$9,$A99,'Entrega'!$E$6:$E$9,"Ambos")+SUMIFS('Defensa'!$I$6:$I$10,'Defensa'!$B$6:$B$10,$A99,'Defensa'!$E$6:$E$10,"Víctor")+SUMIFS('Defensa'!$I$6:$I$10,'Defensa'!$B$6:$B$10,$A99,'Defensa'!$E$6:$E$10,"Ambos")</f>
         <v/>
       </c>
       <c r="E99" s="21">
-        <f>SUMIFS('S1'!$I$6:$I$32,'S1'!$B$6:$B$32,$A99,'S1'!$E$6:$E$32,"Diego")+SUMIFS('S1'!$I$6:$I$32,'S1'!$B$6:$B$32,$A99,'S1'!$E$6:$E$32,"Ambos")+SUMIFS('S2'!$I$6:$I$23,'S2'!$B$6:$B$23,$A99,'S2'!$E$6:$E$23,"Diego")+SUMIFS('S2'!$I$6:$I$23,'S2'!$B$6:$B$23,$A99,'S2'!$E$6:$E$23,"Ambos")+SUMIFS('S3'!$I$6:$I$19,'S3'!$B$6:$B$19,$A99,'S3'!$E$6:$E$19,"Diego")+SUMIFS('S3'!$I$6:$I$19,'S3'!$B$6:$B$19,$A99,'S3'!$E$6:$E$19,"Ambos")+SUMIFS('S4'!$I$6:$I$20,'S4'!$B$6:$B$20,$A99,'S4'!$E$6:$E$20,"Diego")+SUMIFS('S4'!$I$6:$I$20,'S4'!$B$6:$B$20,$A99,'S4'!$E$6:$E$20,"Ambos")+SUMIFS('S5'!$I$6:$I$20,'S5'!$B$6:$B$20,$A99,'S5'!$E$6:$E$20,"Diego")+SUMIFS('S5'!$I$6:$I$20,'S5'!$B$6:$B$20,$A99,'S5'!$E$6:$E$20,"Ambos")+SUMIFS('S6'!$I$6:$I$17,'S6'!$B$6:$B$17,$A99,'S6'!$E$6:$E$17,"Diego")+SUMIFS('S6'!$I$6:$I$17,'S6'!$B$6:$B$17,$A99,'S6'!$E$6:$E$17,"Ambos")+SUMIFS('S7'!$I$6:$I$19,'S7'!$B$6:$B$19,$A99,'S7'!$E$6:$E$19,"Diego")+SUMIFS('S7'!$I$6:$I$19,'S7'!$B$6:$B$19,$A99,'S7'!$E$6:$E$19,"Ambos")+SUMIFS('S8'!$I$6:$I$23,'S8'!$B$6:$B$23,$A99,'S8'!$E$6:$E$23,"Diego")+SUMIFS('S8'!$I$6:$I$23,'S8'!$B$6:$B$23,$A99,'S8'!$E$6:$E$23,"Ambos")+SUMIFS('S9'!$I$6:$I$15,'S9'!$B$6:$B$15,$A99,'S9'!$E$6:$E$15,"Diego")+SUMIFS('S9'!$I$6:$I$15,'S9'!$B$6:$B$15,$A99,'S9'!$E$6:$E$15,"Ambos")+SUMIFS('S10'!$I$6:$I$13,'S10'!$B$6:$B$13,$A99,'S10'!$E$6:$E$13,"Diego")+SUMIFS('S10'!$I$6:$I$13,'S10'!$B$6:$B$13,$A99,'S10'!$E$6:$E$13,"Ambos")+SUMIFS('Holgura'!$I$6:$I$11,'Holgura'!$B$6:$B$11,$A99,'Holgura'!$E$6:$E$11,"Diego")+SUMIFS('Holgura'!$I$6:$I$11,'Holgura'!$B$6:$B$11,$A99,'Holgura'!$E$6:$E$11,"Ambos")+SUMIFS('Entrega'!$I$6:$I$9,'Entrega'!$B$6:$B$9,$A99,'Entrega'!$E$6:$E$9,"Diego")+SUMIFS('Entrega'!$I$6:$I$9,'Entrega'!$B$6:$B$9,$A99,'Entrega'!$E$6:$E$9,"Ambos")+SUMIFS('Defensa'!$I$6:$I$10,'Defensa'!$B$6:$B$10,$A99,'Defensa'!$E$6:$E$10,"Diego")+SUMIFS('Defensa'!$I$6:$I$10,'Defensa'!$B$6:$B$10,$A99,'Defensa'!$E$6:$E$10,"Ambos")</f>
+        <f>SUMIFS('S1'!$I$6:$I$32,'S1'!$B$6:$B$32,$A99,'S1'!$E$6:$E$32,"Diego")+SUMIFS('S1'!$I$6:$I$32,'S1'!$B$6:$B$32,$A99,'S1'!$E$6:$E$32,"Ambos")+SUMIFS('S2'!$I$6:$I$23,'S2'!$B$6:$B$23,$A99,'S2'!$E$6:$E$23,"Diego")+SUMIFS('S2'!$I$6:$I$23,'S2'!$B$6:$B$23,$A99,'S2'!$E$6:$E$23,"Ambos")+SUMIFS('S3'!$I$6:$I$24,'S3'!$B$6:$B$24,$A99,'S3'!$E$6:$E$24,"Diego")+SUMIFS('S3'!$I$6:$I$24,'S3'!$B$6:$B$24,$A99,'S3'!$E$6:$E$24,"Ambos")+SUMIFS('S4'!$I$6:$I$22,'S4'!$B$6:$B$22,$A99,'S4'!$E$6:$E$22,"Diego")+SUMIFS('S4'!$I$6:$I$22,'S4'!$B$6:$B$22,$A99,'S4'!$E$6:$E$22,"Ambos")+SUMIFS('S5'!$I$6:$I$20,'S5'!$B$6:$B$20,$A99,'S5'!$E$6:$E$20,"Diego")+SUMIFS('S5'!$I$6:$I$20,'S5'!$B$6:$B$20,$A99,'S5'!$E$6:$E$20,"Ambos")+SUMIFS('S6'!$I$6:$I$17,'S6'!$B$6:$B$17,$A99,'S6'!$E$6:$E$17,"Diego")+SUMIFS('S6'!$I$6:$I$17,'S6'!$B$6:$B$17,$A99,'S6'!$E$6:$E$17,"Ambos")+SUMIFS('S7'!$I$6:$I$19,'S7'!$B$6:$B$19,$A99,'S7'!$E$6:$E$19,"Diego")+SUMIFS('S7'!$I$6:$I$19,'S7'!$B$6:$B$19,$A99,'S7'!$E$6:$E$19,"Ambos")+SUMIFS('S8'!$I$6:$I$23,'S8'!$B$6:$B$23,$A99,'S8'!$E$6:$E$23,"Diego")+SUMIFS('S8'!$I$6:$I$23,'S8'!$B$6:$B$23,$A99,'S8'!$E$6:$E$23,"Ambos")+SUMIFS('S9'!$I$6:$I$15,'S9'!$B$6:$B$15,$A99,'S9'!$E$6:$E$15,"Diego")+SUMIFS('S9'!$I$6:$I$15,'S9'!$B$6:$B$15,$A99,'S9'!$E$6:$E$15,"Ambos")+SUMIFS('S10'!$I$6:$I$13,'S10'!$B$6:$B$13,$A99,'S10'!$E$6:$E$13,"Diego")+SUMIFS('S10'!$I$6:$I$13,'S10'!$B$6:$B$13,$A99,'S10'!$E$6:$E$13,"Ambos")+SUMIFS('Holgura'!$I$6:$I$11,'Holgura'!$B$6:$B$11,$A99,'Holgura'!$E$6:$E$11,"Diego")+SUMIFS('Holgura'!$I$6:$I$11,'Holgura'!$B$6:$B$11,$A99,'Holgura'!$E$6:$E$11,"Ambos")+SUMIFS('Entrega'!$I$6:$I$9,'Entrega'!$B$6:$B$9,$A99,'Entrega'!$E$6:$E$9,"Diego")+SUMIFS('Entrega'!$I$6:$I$9,'Entrega'!$B$6:$B$9,$A99,'Entrega'!$E$6:$E$9,"Ambos")+SUMIFS('Defensa'!$I$6:$I$10,'Defensa'!$B$6:$B$10,$A99,'Defensa'!$E$6:$E$10,"Diego")+SUMIFS('Defensa'!$I$6:$I$10,'Defensa'!$B$6:$B$10,$A99,'Defensa'!$E$6:$E$10,"Ambos")</f>
         <v/>
       </c>
       <c r="F99" s="21">
-        <f>COUNTIFS('S1'!$B$6:$B$32,$A99,'S1'!$E$6:$E$32,"Víctor")+COUNTIFS('S1'!$B$6:$B$32,$A99,'S1'!$E$6:$E$32,"Ambos")+COUNTIFS('S2'!$B$6:$B$23,$A99,'S2'!$E$6:$E$23,"Víctor")+COUNTIFS('S2'!$B$6:$B$23,$A99,'S2'!$E$6:$E$23,"Ambos")+COUNTIFS('S3'!$B$6:$B$19,$A99,'S3'!$E$6:$E$19,"Víctor")+COUNTIFS('S3'!$B$6:$B$19,$A99,'S3'!$E$6:$E$19,"Ambos")+COUNTIFS('S4'!$B$6:$B$20,$A99,'S4'!$E$6:$E$20,"Víctor")+COUNTIFS('S4'!$B$6:$B$20,$A99,'S4'!$E$6:$E$20,"Ambos")+COUNTIFS('S5'!$B$6:$B$20,$A99,'S5'!$E$6:$E$20,"Víctor")+COUNTIFS('S5'!$B$6:$B$20,$A99,'S5'!$E$6:$E$20,"Ambos")+COUNTIFS('S6'!$B$6:$B$17,$A99,'S6'!$E$6:$E$17,"Víctor")+COUNTIFS('S6'!$B$6:$B$17,$A99,'S6'!$E$6:$E$17,"Ambos")+COUNTIFS('S7'!$B$6:$B$19,$A99,'S7'!$E$6:$E$19,"Víctor")+COUNTIFS('S7'!$B$6:$B$19,$A99,'S7'!$E$6:$E$19,"Ambos")+COUNTIFS('S8'!$B$6:$B$23,$A99,'S8'!$E$6:$E$23,"Víctor")+COUNTIFS('S8'!$B$6:$B$23,$A99,'S8'!$E$6:$E$23,"Ambos")+COUNTIFS('S9'!$B$6:$B$15,$A99,'S9'!$E$6:$E$15,"Víctor")+COUNTIFS('S9'!$B$6:$B$15,$A99,'S9'!$E$6:$E$15,"Ambos")+COUNTIFS('S10'!$B$6:$B$13,$A99,'S10'!$E$6:$E$13,"Víctor")+COUNTIFS('S10'!$B$6:$B$13,$A99,'S10'!$E$6:$E$13,"Ambos")+COUNTIFS('Holgura'!$B$6:$B$11,$A99,'Holgura'!$E$6:$E$11,"Víctor")+COUNTIFS('Holgura'!$B$6:$B$11,$A99,'Holgura'!$E$6:$E$11,"Ambos")+COUNTIFS('Entrega'!$B$6:$B$9,$A99,'Entrega'!$E$6:$E$9,"Víctor")+COUNTIFS('Entrega'!$B$6:$B$9,$A99,'Entrega'!$E$6:$E$9,"Ambos")+COUNTIFS('Defensa'!$B$6:$B$10,$A99,'Defensa'!$E$6:$E$10,"Víctor")+COUNTIFS('Defensa'!$B$6:$B$10,$A99,'Defensa'!$E$6:$E$10,"Ambos")</f>
+        <f>COUNTIFS('S1'!$B$6:$B$32,$A99,'S1'!$E$6:$E$32,"Víctor")+COUNTIFS('S1'!$B$6:$B$32,$A99,'S1'!$E$6:$E$32,"Ambos")+COUNTIFS('S2'!$B$6:$B$23,$A99,'S2'!$E$6:$E$23,"Víctor")+COUNTIFS('S2'!$B$6:$B$23,$A99,'S2'!$E$6:$E$23,"Ambos")+COUNTIFS('S3'!$B$6:$B$24,$A99,'S3'!$E$6:$E$24,"Víctor")+COUNTIFS('S3'!$B$6:$B$24,$A99,'S3'!$E$6:$E$24,"Ambos")+COUNTIFS('S4'!$B$6:$B$22,$A99,'S4'!$E$6:$E$22,"Víctor")+COUNTIFS('S4'!$B$6:$B$22,$A99,'S4'!$E$6:$E$22,"Ambos")+COUNTIFS('S5'!$B$6:$B$20,$A99,'S5'!$E$6:$E$20,"Víctor")+COUNTIFS('S5'!$B$6:$B$20,$A99,'S5'!$E$6:$E$20,"Ambos")+COUNTIFS('S6'!$B$6:$B$17,$A99,'S6'!$E$6:$E$17,"Víctor")+COUNTIFS('S6'!$B$6:$B$17,$A99,'S6'!$E$6:$E$17,"Ambos")+COUNTIFS('S7'!$B$6:$B$19,$A99,'S7'!$E$6:$E$19,"Víctor")+COUNTIFS('S7'!$B$6:$B$19,$A99,'S7'!$E$6:$E$19,"Ambos")+COUNTIFS('S8'!$B$6:$B$23,$A99,'S8'!$E$6:$E$23,"Víctor")+COUNTIFS('S8'!$B$6:$B$23,$A99,'S8'!$E$6:$E$23,"Ambos")+COUNTIFS('S9'!$B$6:$B$15,$A99,'S9'!$E$6:$E$15,"Víctor")+COUNTIFS('S9'!$B$6:$B$15,$A99,'S9'!$E$6:$E$15,"Ambos")+COUNTIFS('S10'!$B$6:$B$13,$A99,'S10'!$E$6:$E$13,"Víctor")+COUNTIFS('S10'!$B$6:$B$13,$A99,'S10'!$E$6:$E$13,"Ambos")+COUNTIFS('Holgura'!$B$6:$B$11,$A99,'Holgura'!$E$6:$E$11,"Víctor")+COUNTIFS('Holgura'!$B$6:$B$11,$A99,'Holgura'!$E$6:$E$11,"Ambos")+COUNTIFS('Entrega'!$B$6:$B$9,$A99,'Entrega'!$E$6:$E$9,"Víctor")+COUNTIFS('Entrega'!$B$6:$B$9,$A99,'Entrega'!$E$6:$E$9,"Ambos")+COUNTIFS('Defensa'!$B$6:$B$10,$A99,'Defensa'!$E$6:$E$10,"Víctor")+COUNTIFS('Defensa'!$B$6:$B$10,$A99,'Defensa'!$E$6:$E$10,"Ambos")</f>
         <v/>
       </c>
       <c r="G99" s="21">
-        <f>COUNTIFS('S1'!$B$6:$B$32,$A99,'S1'!$E$6:$E$32,"Diego")+COUNTIFS('S1'!$B$6:$B$32,$A99,'S1'!$E$6:$E$32,"Ambos")+COUNTIFS('S2'!$B$6:$B$23,$A99,'S2'!$E$6:$E$23,"Diego")+COUNTIFS('S2'!$B$6:$B$23,$A99,'S2'!$E$6:$E$23,"Ambos")+COUNTIFS('S3'!$B$6:$B$19,$A99,'S3'!$E$6:$E$19,"Diego")+COUNTIFS('S3'!$B$6:$B$19,$A99,'S3'!$E$6:$E$19,"Ambos")+COUNTIFS('S4'!$B$6:$B$20,$A99,'S4'!$E$6:$E$20,"Diego")+COUNTIFS('S4'!$B$6:$B$20,$A99,'S4'!$E$6:$E$20,"Ambos")+COUNTIFS('S5'!$B$6:$B$20,$A99,'S5'!$E$6:$E$20,"Diego")+COUNTIFS('S5'!$B$6:$B$20,$A99,'S5'!$E$6:$E$20,"Ambos")+COUNTIFS('S6'!$B$6:$B$17,$A99,'S6'!$E$6:$E$17,"Diego")+COUNTIFS('S6'!$B$6:$B$17,$A99,'S6'!$E$6:$E$17,"Ambos")+COUNTIFS('S7'!$B$6:$B$19,$A99,'S7'!$E$6:$E$19,"Diego")+COUNTIFS('S7'!$B$6:$B$19,$A99,'S7'!$E$6:$E$19,"Ambos")+COUNTIFS('S8'!$B$6:$B$23,$A99,'S8'!$E$6:$E$23,"Diego")+COUNTIFS('S8'!$B$6:$B$23,$A99,'S8'!$E$6:$E$23,"Ambos")+COUNTIFS('S9'!$B$6:$B$15,$A99,'S9'!$E$6:$E$15,"Diego")+COUNTIFS('S9'!$B$6:$B$15,$A99,'S9'!$E$6:$E$15,"Ambos")+COUNTIFS('S10'!$B$6:$B$13,$A99,'S10'!$E$6:$E$13,"Diego")+COUNTIFS('S10'!$B$6:$B$13,$A99,'S10'!$E$6:$E$13,"Ambos")+COUNTIFS('Holgura'!$B$6:$B$11,$A99,'Holgura'!$E$6:$E$11,"Diego")+COUNTIFS('Holgura'!$B$6:$B$11,$A99,'Holgura'!$E$6:$E$11,"Ambos")+COUNTIFS('Entrega'!$B$6:$B$9,$A99,'Entrega'!$E$6:$E$9,"Diego")+COUNTIFS('Entrega'!$B$6:$B$9,$A99,'Entrega'!$E$6:$E$9,"Ambos")+COUNTIFS('Defensa'!$B$6:$B$10,$A99,'Defensa'!$E$6:$E$10,"Diego")+COUNTIFS('Defensa'!$B$6:$B$10,$A99,'Defensa'!$E$6:$E$10,"Ambos")</f>
+        <f>COUNTIFS('S1'!$B$6:$B$32,$A99,'S1'!$E$6:$E$32,"Diego")+COUNTIFS('S1'!$B$6:$B$32,$A99,'S1'!$E$6:$E$32,"Ambos")+COUNTIFS('S2'!$B$6:$B$23,$A99,'S2'!$E$6:$E$23,"Diego")+COUNTIFS('S2'!$B$6:$B$23,$A99,'S2'!$E$6:$E$23,"Ambos")+COUNTIFS('S3'!$B$6:$B$24,$A99,'S3'!$E$6:$E$24,"Diego")+COUNTIFS('S3'!$B$6:$B$24,$A99,'S3'!$E$6:$E$24,"Ambos")+COUNTIFS('S4'!$B$6:$B$22,$A99,'S4'!$E$6:$E$22,"Diego")+COUNTIFS('S4'!$B$6:$B$22,$A99,'S4'!$E$6:$E$22,"Ambos")+COUNTIFS('S5'!$B$6:$B$20,$A99,'S5'!$E$6:$E$20,"Diego")+COUNTIFS('S5'!$B$6:$B$20,$A99,'S5'!$E$6:$E$20,"Ambos")+COUNTIFS('S6'!$B$6:$B$17,$A99,'S6'!$E$6:$E$17,"Diego")+COUNTIFS('S6'!$B$6:$B$17,$A99,'S6'!$E$6:$E$17,"Ambos")+COUNTIFS('S7'!$B$6:$B$19,$A99,'S7'!$E$6:$E$19,"Diego")+COUNTIFS('S7'!$B$6:$B$19,$A99,'S7'!$E$6:$E$19,"Ambos")+COUNTIFS('S8'!$B$6:$B$23,$A99,'S8'!$E$6:$E$23,"Diego")+COUNTIFS('S8'!$B$6:$B$23,$A99,'S8'!$E$6:$E$23,"Ambos")+COUNTIFS('S9'!$B$6:$B$15,$A99,'S9'!$E$6:$E$15,"Diego")+COUNTIFS('S9'!$B$6:$B$15,$A99,'S9'!$E$6:$E$15,"Ambos")+COUNTIFS('S10'!$B$6:$B$13,$A99,'S10'!$E$6:$E$13,"Diego")+COUNTIFS('S10'!$B$6:$B$13,$A99,'S10'!$E$6:$E$13,"Ambos")+COUNTIFS('Holgura'!$B$6:$B$11,$A99,'Holgura'!$E$6:$E$11,"Diego")+COUNTIFS('Holgura'!$B$6:$B$11,$A99,'Holgura'!$E$6:$E$11,"Ambos")+COUNTIFS('Entrega'!$B$6:$B$9,$A99,'Entrega'!$E$6:$E$9,"Diego")+COUNTIFS('Entrega'!$B$6:$B$9,$A99,'Entrega'!$E$6:$E$9,"Ambos")+COUNTIFS('Defensa'!$B$6:$B$10,$A99,'Defensa'!$E$6:$E$10,"Diego")+COUNTIFS('Defensa'!$B$6:$B$10,$A99,'Defensa'!$E$6:$E$10,"Ambos")</f>
         <v/>
       </c>
     </row>
@@ -11435,19 +11456,19 @@
         <v/>
       </c>
       <c r="D100" s="21">
-        <f>SUMIFS('S1'!$I$6:$I$32,'S1'!$B$6:$B$32,$A100,'S1'!$E$6:$E$32,"Víctor")+SUMIFS('S1'!$I$6:$I$32,'S1'!$B$6:$B$32,$A100,'S1'!$E$6:$E$32,"Ambos")+SUMIFS('S2'!$I$6:$I$23,'S2'!$B$6:$B$23,$A100,'S2'!$E$6:$E$23,"Víctor")+SUMIFS('S2'!$I$6:$I$23,'S2'!$B$6:$B$23,$A100,'S2'!$E$6:$E$23,"Ambos")+SUMIFS('S3'!$I$6:$I$19,'S3'!$B$6:$B$19,$A100,'S3'!$E$6:$E$19,"Víctor")+SUMIFS('S3'!$I$6:$I$19,'S3'!$B$6:$B$19,$A100,'S3'!$E$6:$E$19,"Ambos")+SUMIFS('S4'!$I$6:$I$20,'S4'!$B$6:$B$20,$A100,'S4'!$E$6:$E$20,"Víctor")+SUMIFS('S4'!$I$6:$I$20,'S4'!$B$6:$B$20,$A100,'S4'!$E$6:$E$20,"Ambos")+SUMIFS('S5'!$I$6:$I$20,'S5'!$B$6:$B$20,$A100,'S5'!$E$6:$E$20,"Víctor")+SUMIFS('S5'!$I$6:$I$20,'S5'!$B$6:$B$20,$A100,'S5'!$E$6:$E$20,"Ambos")+SUMIFS('S6'!$I$6:$I$17,'S6'!$B$6:$B$17,$A100,'S6'!$E$6:$E$17,"Víctor")+SUMIFS('S6'!$I$6:$I$17,'S6'!$B$6:$B$17,$A100,'S6'!$E$6:$E$17,"Ambos")+SUMIFS('S7'!$I$6:$I$19,'S7'!$B$6:$B$19,$A100,'S7'!$E$6:$E$19,"Víctor")+SUMIFS('S7'!$I$6:$I$19,'S7'!$B$6:$B$19,$A100,'S7'!$E$6:$E$19,"Ambos")+SUMIFS('S8'!$I$6:$I$23,'S8'!$B$6:$B$23,$A100,'S8'!$E$6:$E$23,"Víctor")+SUMIFS('S8'!$I$6:$I$23,'S8'!$B$6:$B$23,$A100,'S8'!$E$6:$E$23,"Ambos")+SUMIFS('S9'!$I$6:$I$15,'S9'!$B$6:$B$15,$A100,'S9'!$E$6:$E$15,"Víctor")+SUMIFS('S9'!$I$6:$I$15,'S9'!$B$6:$B$15,$A100,'S9'!$E$6:$E$15,"Ambos")+SUMIFS('S10'!$I$6:$I$13,'S10'!$B$6:$B$13,$A100,'S10'!$E$6:$E$13,"Víctor")+SUMIFS('S10'!$I$6:$I$13,'S10'!$B$6:$B$13,$A100,'S10'!$E$6:$E$13,"Ambos")+SUMIFS('Holgura'!$I$6:$I$11,'Holgura'!$B$6:$B$11,$A100,'Holgura'!$E$6:$E$11,"Víctor")+SUMIFS('Holgura'!$I$6:$I$11,'Holgura'!$B$6:$B$11,$A100,'Holgura'!$E$6:$E$11,"Ambos")+SUMIFS('Entrega'!$I$6:$I$9,'Entrega'!$B$6:$B$9,$A100,'Entrega'!$E$6:$E$9,"Víctor")+SUMIFS('Entrega'!$I$6:$I$9,'Entrega'!$B$6:$B$9,$A100,'Entrega'!$E$6:$E$9,"Ambos")+SUMIFS('Defensa'!$I$6:$I$10,'Defensa'!$B$6:$B$10,$A100,'Defensa'!$E$6:$E$10,"Víctor")+SUMIFS('Defensa'!$I$6:$I$10,'Defensa'!$B$6:$B$10,$A100,'Defensa'!$E$6:$E$10,"Ambos")</f>
+        <f>SUMIFS('S1'!$I$6:$I$32,'S1'!$B$6:$B$32,$A100,'S1'!$E$6:$E$32,"Víctor")+SUMIFS('S1'!$I$6:$I$32,'S1'!$B$6:$B$32,$A100,'S1'!$E$6:$E$32,"Ambos")+SUMIFS('S2'!$I$6:$I$23,'S2'!$B$6:$B$23,$A100,'S2'!$E$6:$E$23,"Víctor")+SUMIFS('S2'!$I$6:$I$23,'S2'!$B$6:$B$23,$A100,'S2'!$E$6:$E$23,"Ambos")+SUMIFS('S3'!$I$6:$I$24,'S3'!$B$6:$B$24,$A100,'S3'!$E$6:$E$24,"Víctor")+SUMIFS('S3'!$I$6:$I$24,'S3'!$B$6:$B$24,$A100,'S3'!$E$6:$E$24,"Ambos")+SUMIFS('S4'!$I$6:$I$22,'S4'!$B$6:$B$22,$A100,'S4'!$E$6:$E$22,"Víctor")+SUMIFS('S4'!$I$6:$I$22,'S4'!$B$6:$B$22,$A100,'S4'!$E$6:$E$22,"Ambos")+SUMIFS('S5'!$I$6:$I$20,'S5'!$B$6:$B$20,$A100,'S5'!$E$6:$E$20,"Víctor")+SUMIFS('S5'!$I$6:$I$20,'S5'!$B$6:$B$20,$A100,'S5'!$E$6:$E$20,"Ambos")+SUMIFS('S6'!$I$6:$I$17,'S6'!$B$6:$B$17,$A100,'S6'!$E$6:$E$17,"Víctor")+SUMIFS('S6'!$I$6:$I$17,'S6'!$B$6:$B$17,$A100,'S6'!$E$6:$E$17,"Ambos")+SUMIFS('S7'!$I$6:$I$19,'S7'!$B$6:$B$19,$A100,'S7'!$E$6:$E$19,"Víctor")+SUMIFS('S7'!$I$6:$I$19,'S7'!$B$6:$B$19,$A100,'S7'!$E$6:$E$19,"Ambos")+SUMIFS('S8'!$I$6:$I$23,'S8'!$B$6:$B$23,$A100,'S8'!$E$6:$E$23,"Víctor")+SUMIFS('S8'!$I$6:$I$23,'S8'!$B$6:$B$23,$A100,'S8'!$E$6:$E$23,"Ambos")+SUMIFS('S9'!$I$6:$I$15,'S9'!$B$6:$B$15,$A100,'S9'!$E$6:$E$15,"Víctor")+SUMIFS('S9'!$I$6:$I$15,'S9'!$B$6:$B$15,$A100,'S9'!$E$6:$E$15,"Ambos")+SUMIFS('S10'!$I$6:$I$13,'S10'!$B$6:$B$13,$A100,'S10'!$E$6:$E$13,"Víctor")+SUMIFS('S10'!$I$6:$I$13,'S10'!$B$6:$B$13,$A100,'S10'!$E$6:$E$13,"Ambos")+SUMIFS('Holgura'!$I$6:$I$11,'Holgura'!$B$6:$B$11,$A100,'Holgura'!$E$6:$E$11,"Víctor")+SUMIFS('Holgura'!$I$6:$I$11,'Holgura'!$B$6:$B$11,$A100,'Holgura'!$E$6:$E$11,"Ambos")+SUMIFS('Entrega'!$I$6:$I$9,'Entrega'!$B$6:$B$9,$A100,'Entrega'!$E$6:$E$9,"Víctor")+SUMIFS('Entrega'!$I$6:$I$9,'Entrega'!$B$6:$B$9,$A100,'Entrega'!$E$6:$E$9,"Ambos")+SUMIFS('Defensa'!$I$6:$I$10,'Defensa'!$B$6:$B$10,$A100,'Defensa'!$E$6:$E$10,"Víctor")+SUMIFS('Defensa'!$I$6:$I$10,'Defensa'!$B$6:$B$10,$A100,'Defensa'!$E$6:$E$10,"Ambos")</f>
         <v/>
       </c>
       <c r="E100" s="21">
-        <f>SUMIFS('S1'!$I$6:$I$32,'S1'!$B$6:$B$32,$A100,'S1'!$E$6:$E$32,"Diego")+SUMIFS('S1'!$I$6:$I$32,'S1'!$B$6:$B$32,$A100,'S1'!$E$6:$E$32,"Ambos")+SUMIFS('S2'!$I$6:$I$23,'S2'!$B$6:$B$23,$A100,'S2'!$E$6:$E$23,"Diego")+SUMIFS('S2'!$I$6:$I$23,'S2'!$B$6:$B$23,$A100,'S2'!$E$6:$E$23,"Ambos")+SUMIFS('S3'!$I$6:$I$19,'S3'!$B$6:$B$19,$A100,'S3'!$E$6:$E$19,"Diego")+SUMIFS('S3'!$I$6:$I$19,'S3'!$B$6:$B$19,$A100,'S3'!$E$6:$E$19,"Ambos")+SUMIFS('S4'!$I$6:$I$20,'S4'!$B$6:$B$20,$A100,'S4'!$E$6:$E$20,"Diego")+SUMIFS('S4'!$I$6:$I$20,'S4'!$B$6:$B$20,$A100,'S4'!$E$6:$E$20,"Ambos")+SUMIFS('S5'!$I$6:$I$20,'S5'!$B$6:$B$20,$A100,'S5'!$E$6:$E$20,"Diego")+SUMIFS('S5'!$I$6:$I$20,'S5'!$B$6:$B$20,$A100,'S5'!$E$6:$E$20,"Ambos")+SUMIFS('S6'!$I$6:$I$17,'S6'!$B$6:$B$17,$A100,'S6'!$E$6:$E$17,"Diego")+SUMIFS('S6'!$I$6:$I$17,'S6'!$B$6:$B$17,$A100,'S6'!$E$6:$E$17,"Ambos")+SUMIFS('S7'!$I$6:$I$19,'S7'!$B$6:$B$19,$A100,'S7'!$E$6:$E$19,"Diego")+SUMIFS('S7'!$I$6:$I$19,'S7'!$B$6:$B$19,$A100,'S7'!$E$6:$E$19,"Ambos")+SUMIFS('S8'!$I$6:$I$23,'S8'!$B$6:$B$23,$A100,'S8'!$E$6:$E$23,"Diego")+SUMIFS('S8'!$I$6:$I$23,'S8'!$B$6:$B$23,$A100,'S8'!$E$6:$E$23,"Ambos")+SUMIFS('S9'!$I$6:$I$15,'S9'!$B$6:$B$15,$A100,'S9'!$E$6:$E$15,"Diego")+SUMIFS('S9'!$I$6:$I$15,'S9'!$B$6:$B$15,$A100,'S9'!$E$6:$E$15,"Ambos")+SUMIFS('S10'!$I$6:$I$13,'S10'!$B$6:$B$13,$A100,'S10'!$E$6:$E$13,"Diego")+SUMIFS('S10'!$I$6:$I$13,'S10'!$B$6:$B$13,$A100,'S10'!$E$6:$E$13,"Ambos")+SUMIFS('Holgura'!$I$6:$I$11,'Holgura'!$B$6:$B$11,$A100,'Holgura'!$E$6:$E$11,"Diego")+SUMIFS('Holgura'!$I$6:$I$11,'Holgura'!$B$6:$B$11,$A100,'Holgura'!$E$6:$E$11,"Ambos")+SUMIFS('Entrega'!$I$6:$I$9,'Entrega'!$B$6:$B$9,$A100,'Entrega'!$E$6:$E$9,"Diego")+SUMIFS('Entrega'!$I$6:$I$9,'Entrega'!$B$6:$B$9,$A100,'Entrega'!$E$6:$E$9,"Ambos")+SUMIFS('Defensa'!$I$6:$I$10,'Defensa'!$B$6:$B$10,$A100,'Defensa'!$E$6:$E$10,"Diego")+SUMIFS('Defensa'!$I$6:$I$10,'Defensa'!$B$6:$B$10,$A100,'Defensa'!$E$6:$E$10,"Ambos")</f>
+        <f>SUMIFS('S1'!$I$6:$I$32,'S1'!$B$6:$B$32,$A100,'S1'!$E$6:$E$32,"Diego")+SUMIFS('S1'!$I$6:$I$32,'S1'!$B$6:$B$32,$A100,'S1'!$E$6:$E$32,"Ambos")+SUMIFS('S2'!$I$6:$I$23,'S2'!$B$6:$B$23,$A100,'S2'!$E$6:$E$23,"Diego")+SUMIFS('S2'!$I$6:$I$23,'S2'!$B$6:$B$23,$A100,'S2'!$E$6:$E$23,"Ambos")+SUMIFS('S3'!$I$6:$I$24,'S3'!$B$6:$B$24,$A100,'S3'!$E$6:$E$24,"Diego")+SUMIFS('S3'!$I$6:$I$24,'S3'!$B$6:$B$24,$A100,'S3'!$E$6:$E$24,"Ambos")+SUMIFS('S4'!$I$6:$I$22,'S4'!$B$6:$B$22,$A100,'S4'!$E$6:$E$22,"Diego")+SUMIFS('S4'!$I$6:$I$22,'S4'!$B$6:$B$22,$A100,'S4'!$E$6:$E$22,"Ambos")+SUMIFS('S5'!$I$6:$I$20,'S5'!$B$6:$B$20,$A100,'S5'!$E$6:$E$20,"Diego")+SUMIFS('S5'!$I$6:$I$20,'S5'!$B$6:$B$20,$A100,'S5'!$E$6:$E$20,"Ambos")+SUMIFS('S6'!$I$6:$I$17,'S6'!$B$6:$B$17,$A100,'S6'!$E$6:$E$17,"Diego")+SUMIFS('S6'!$I$6:$I$17,'S6'!$B$6:$B$17,$A100,'S6'!$E$6:$E$17,"Ambos")+SUMIFS('S7'!$I$6:$I$19,'S7'!$B$6:$B$19,$A100,'S7'!$E$6:$E$19,"Diego")+SUMIFS('S7'!$I$6:$I$19,'S7'!$B$6:$B$19,$A100,'S7'!$E$6:$E$19,"Ambos")+SUMIFS('S8'!$I$6:$I$23,'S8'!$B$6:$B$23,$A100,'S8'!$E$6:$E$23,"Diego")+SUMIFS('S8'!$I$6:$I$23,'S8'!$B$6:$B$23,$A100,'S8'!$E$6:$E$23,"Ambos")+SUMIFS('S9'!$I$6:$I$15,'S9'!$B$6:$B$15,$A100,'S9'!$E$6:$E$15,"Diego")+SUMIFS('S9'!$I$6:$I$15,'S9'!$B$6:$B$15,$A100,'S9'!$E$6:$E$15,"Ambos")+SUMIFS('S10'!$I$6:$I$13,'S10'!$B$6:$B$13,$A100,'S10'!$E$6:$E$13,"Diego")+SUMIFS('S10'!$I$6:$I$13,'S10'!$B$6:$B$13,$A100,'S10'!$E$6:$E$13,"Ambos")+SUMIFS('Holgura'!$I$6:$I$11,'Holgura'!$B$6:$B$11,$A100,'Holgura'!$E$6:$E$11,"Diego")+SUMIFS('Holgura'!$I$6:$I$11,'Holgura'!$B$6:$B$11,$A100,'Holgura'!$E$6:$E$11,"Ambos")+SUMIFS('Entrega'!$I$6:$I$9,'Entrega'!$B$6:$B$9,$A100,'Entrega'!$E$6:$E$9,"Diego")+SUMIFS('Entrega'!$I$6:$I$9,'Entrega'!$B$6:$B$9,$A100,'Entrega'!$E$6:$E$9,"Ambos")+SUMIFS('Defensa'!$I$6:$I$10,'Defensa'!$B$6:$B$10,$A100,'Defensa'!$E$6:$E$10,"Diego")+SUMIFS('Defensa'!$I$6:$I$10,'Defensa'!$B$6:$B$10,$A100,'Defensa'!$E$6:$E$10,"Ambos")</f>
         <v/>
       </c>
       <c r="F100" s="21">
-        <f>COUNTIFS('S1'!$B$6:$B$32,$A100,'S1'!$E$6:$E$32,"Víctor")+COUNTIFS('S1'!$B$6:$B$32,$A100,'S1'!$E$6:$E$32,"Ambos")+COUNTIFS('S2'!$B$6:$B$23,$A100,'S2'!$E$6:$E$23,"Víctor")+COUNTIFS('S2'!$B$6:$B$23,$A100,'S2'!$E$6:$E$23,"Ambos")+COUNTIFS('S3'!$B$6:$B$19,$A100,'S3'!$E$6:$E$19,"Víctor")+COUNTIFS('S3'!$B$6:$B$19,$A100,'S3'!$E$6:$E$19,"Ambos")+COUNTIFS('S4'!$B$6:$B$20,$A100,'S4'!$E$6:$E$20,"Víctor")+COUNTIFS('S4'!$B$6:$B$20,$A100,'S4'!$E$6:$E$20,"Ambos")+COUNTIFS('S5'!$B$6:$B$20,$A100,'S5'!$E$6:$E$20,"Víctor")+COUNTIFS('S5'!$B$6:$B$20,$A100,'S5'!$E$6:$E$20,"Ambos")+COUNTIFS('S6'!$B$6:$B$17,$A100,'S6'!$E$6:$E$17,"Víctor")+COUNTIFS('S6'!$B$6:$B$17,$A100,'S6'!$E$6:$E$17,"Ambos")+COUNTIFS('S7'!$B$6:$B$19,$A100,'S7'!$E$6:$E$19,"Víctor")+COUNTIFS('S7'!$B$6:$B$19,$A100,'S7'!$E$6:$E$19,"Ambos")+COUNTIFS('S8'!$B$6:$B$23,$A100,'S8'!$E$6:$E$23,"Víctor")+COUNTIFS('S8'!$B$6:$B$23,$A100,'S8'!$E$6:$E$23,"Ambos")+COUNTIFS('S9'!$B$6:$B$15,$A100,'S9'!$E$6:$E$15,"Víctor")+COUNTIFS('S9'!$B$6:$B$15,$A100,'S9'!$E$6:$E$15,"Ambos")+COUNTIFS('S10'!$B$6:$B$13,$A100,'S10'!$E$6:$E$13,"Víctor")+COUNTIFS('S10'!$B$6:$B$13,$A100,'S10'!$E$6:$E$13,"Ambos")+COUNTIFS('Holgura'!$B$6:$B$11,$A100,'Holgura'!$E$6:$E$11,"Víctor")+COUNTIFS('Holgura'!$B$6:$B$11,$A100,'Holgura'!$E$6:$E$11,"Ambos")+COUNTIFS('Entrega'!$B$6:$B$9,$A100,'Entrega'!$E$6:$E$9,"Víctor")+COUNTIFS('Entrega'!$B$6:$B$9,$A100,'Entrega'!$E$6:$E$9,"Ambos")+COUNTIFS('Defensa'!$B$6:$B$10,$A100,'Defensa'!$E$6:$E$10,"Víctor")+COUNTIFS('Defensa'!$B$6:$B$10,$A100,'Defensa'!$E$6:$E$10,"Ambos")</f>
+        <f>COUNTIFS('S1'!$B$6:$B$32,$A100,'S1'!$E$6:$E$32,"Víctor")+COUNTIFS('S1'!$B$6:$B$32,$A100,'S1'!$E$6:$E$32,"Ambos")+COUNTIFS('S2'!$B$6:$B$23,$A100,'S2'!$E$6:$E$23,"Víctor")+COUNTIFS('S2'!$B$6:$B$23,$A100,'S2'!$E$6:$E$23,"Ambos")+COUNTIFS('S3'!$B$6:$B$24,$A100,'S3'!$E$6:$E$24,"Víctor")+COUNTIFS('S3'!$B$6:$B$24,$A100,'S3'!$E$6:$E$24,"Ambos")+COUNTIFS('S4'!$B$6:$B$22,$A100,'S4'!$E$6:$E$22,"Víctor")+COUNTIFS('S4'!$B$6:$B$22,$A100,'S4'!$E$6:$E$22,"Ambos")+COUNTIFS('S5'!$B$6:$B$20,$A100,'S5'!$E$6:$E$20,"Víctor")+COUNTIFS('S5'!$B$6:$B$20,$A100,'S5'!$E$6:$E$20,"Ambos")+COUNTIFS('S6'!$B$6:$B$17,$A100,'S6'!$E$6:$E$17,"Víctor")+COUNTIFS('S6'!$B$6:$B$17,$A100,'S6'!$E$6:$E$17,"Ambos")+COUNTIFS('S7'!$B$6:$B$19,$A100,'S7'!$E$6:$E$19,"Víctor")+COUNTIFS('S7'!$B$6:$B$19,$A100,'S7'!$E$6:$E$19,"Ambos")+COUNTIFS('S8'!$B$6:$B$23,$A100,'S8'!$E$6:$E$23,"Víctor")+COUNTIFS('S8'!$B$6:$B$23,$A100,'S8'!$E$6:$E$23,"Ambos")+COUNTIFS('S9'!$B$6:$B$15,$A100,'S9'!$E$6:$E$15,"Víctor")+COUNTIFS('S9'!$B$6:$B$15,$A100,'S9'!$E$6:$E$15,"Ambos")+COUNTIFS('S10'!$B$6:$B$13,$A100,'S10'!$E$6:$E$13,"Víctor")+COUNTIFS('S10'!$B$6:$B$13,$A100,'S10'!$E$6:$E$13,"Ambos")+COUNTIFS('Holgura'!$B$6:$B$11,$A100,'Holgura'!$E$6:$E$11,"Víctor")+COUNTIFS('Holgura'!$B$6:$B$11,$A100,'Holgura'!$E$6:$E$11,"Ambos")+COUNTIFS('Entrega'!$B$6:$B$9,$A100,'Entrega'!$E$6:$E$9,"Víctor")+COUNTIFS('Entrega'!$B$6:$B$9,$A100,'Entrega'!$E$6:$E$9,"Ambos")+COUNTIFS('Defensa'!$B$6:$B$10,$A100,'Defensa'!$E$6:$E$10,"Víctor")+COUNTIFS('Defensa'!$B$6:$B$10,$A100,'Defensa'!$E$6:$E$10,"Ambos")</f>
         <v/>
       </c>
       <c r="G100" s="21">
-        <f>COUNTIFS('S1'!$B$6:$B$32,$A100,'S1'!$E$6:$E$32,"Diego")+COUNTIFS('S1'!$B$6:$B$32,$A100,'S1'!$E$6:$E$32,"Ambos")+COUNTIFS('S2'!$B$6:$B$23,$A100,'S2'!$E$6:$E$23,"Diego")+COUNTIFS('S2'!$B$6:$B$23,$A100,'S2'!$E$6:$E$23,"Ambos")+COUNTIFS('S3'!$B$6:$B$19,$A100,'S3'!$E$6:$E$19,"Diego")+COUNTIFS('S3'!$B$6:$B$19,$A100,'S3'!$E$6:$E$19,"Ambos")+COUNTIFS('S4'!$B$6:$B$20,$A100,'S4'!$E$6:$E$20,"Diego")+COUNTIFS('S4'!$B$6:$B$20,$A100,'S4'!$E$6:$E$20,"Ambos")+COUNTIFS('S5'!$B$6:$B$20,$A100,'S5'!$E$6:$E$20,"Diego")+COUNTIFS('S5'!$B$6:$B$20,$A100,'S5'!$E$6:$E$20,"Ambos")+COUNTIFS('S6'!$B$6:$B$17,$A100,'S6'!$E$6:$E$17,"Diego")+COUNTIFS('S6'!$B$6:$B$17,$A100,'S6'!$E$6:$E$17,"Ambos")+COUNTIFS('S7'!$B$6:$B$19,$A100,'S7'!$E$6:$E$19,"Diego")+COUNTIFS('S7'!$B$6:$B$19,$A100,'S7'!$E$6:$E$19,"Ambos")+COUNTIFS('S8'!$B$6:$B$23,$A100,'S8'!$E$6:$E$23,"Diego")+COUNTIFS('S8'!$B$6:$B$23,$A100,'S8'!$E$6:$E$23,"Ambos")+COUNTIFS('S9'!$B$6:$B$15,$A100,'S9'!$E$6:$E$15,"Diego")+COUNTIFS('S9'!$B$6:$B$15,$A100,'S9'!$E$6:$E$15,"Ambos")+COUNTIFS('S10'!$B$6:$B$13,$A100,'S10'!$E$6:$E$13,"Diego")+COUNTIFS('S10'!$B$6:$B$13,$A100,'S10'!$E$6:$E$13,"Ambos")+COUNTIFS('Holgura'!$B$6:$B$11,$A100,'Holgura'!$E$6:$E$11,"Diego")+COUNTIFS('Holgura'!$B$6:$B$11,$A100,'Holgura'!$E$6:$E$11,"Ambos")+COUNTIFS('Entrega'!$B$6:$B$9,$A100,'Entrega'!$E$6:$E$9,"Diego")+COUNTIFS('Entrega'!$B$6:$B$9,$A100,'Entrega'!$E$6:$E$9,"Ambos")+COUNTIFS('Defensa'!$B$6:$B$10,$A100,'Defensa'!$E$6:$E$10,"Diego")+COUNTIFS('Defensa'!$B$6:$B$10,$A100,'Defensa'!$E$6:$E$10,"Ambos")</f>
+        <f>COUNTIFS('S1'!$B$6:$B$32,$A100,'S1'!$E$6:$E$32,"Diego")+COUNTIFS('S1'!$B$6:$B$32,$A100,'S1'!$E$6:$E$32,"Ambos")+COUNTIFS('S2'!$B$6:$B$23,$A100,'S2'!$E$6:$E$23,"Diego")+COUNTIFS('S2'!$B$6:$B$23,$A100,'S2'!$E$6:$E$23,"Ambos")+COUNTIFS('S3'!$B$6:$B$24,$A100,'S3'!$E$6:$E$24,"Diego")+COUNTIFS('S3'!$B$6:$B$24,$A100,'S3'!$E$6:$E$24,"Ambos")+COUNTIFS('S4'!$B$6:$B$22,$A100,'S4'!$E$6:$E$22,"Diego")+COUNTIFS('S4'!$B$6:$B$22,$A100,'S4'!$E$6:$E$22,"Ambos")+COUNTIFS('S5'!$B$6:$B$20,$A100,'S5'!$E$6:$E$20,"Diego")+COUNTIFS('S5'!$B$6:$B$20,$A100,'S5'!$E$6:$E$20,"Ambos")+COUNTIFS('S6'!$B$6:$B$17,$A100,'S6'!$E$6:$E$17,"Diego")+COUNTIFS('S6'!$B$6:$B$17,$A100,'S6'!$E$6:$E$17,"Ambos")+COUNTIFS('S7'!$B$6:$B$19,$A100,'S7'!$E$6:$E$19,"Diego")+COUNTIFS('S7'!$B$6:$B$19,$A100,'S7'!$E$6:$E$19,"Ambos")+COUNTIFS('S8'!$B$6:$B$23,$A100,'S8'!$E$6:$E$23,"Diego")+COUNTIFS('S8'!$B$6:$B$23,$A100,'S8'!$E$6:$E$23,"Ambos")+COUNTIFS('S9'!$B$6:$B$15,$A100,'S9'!$E$6:$E$15,"Diego")+COUNTIFS('S9'!$B$6:$B$15,$A100,'S9'!$E$6:$E$15,"Ambos")+COUNTIFS('S10'!$B$6:$B$13,$A100,'S10'!$E$6:$E$13,"Diego")+COUNTIFS('S10'!$B$6:$B$13,$A100,'S10'!$E$6:$E$13,"Ambos")+COUNTIFS('Holgura'!$B$6:$B$11,$A100,'Holgura'!$E$6:$E$11,"Diego")+COUNTIFS('Holgura'!$B$6:$B$11,$A100,'Holgura'!$E$6:$E$11,"Ambos")+COUNTIFS('Entrega'!$B$6:$B$9,$A100,'Entrega'!$E$6:$E$9,"Diego")+COUNTIFS('Entrega'!$B$6:$B$9,$A100,'Entrega'!$E$6:$E$9,"Ambos")+COUNTIFS('Defensa'!$B$6:$B$10,$A100,'Defensa'!$E$6:$E$10,"Diego")+COUNTIFS('Defensa'!$B$6:$B$10,$A100,'Defensa'!$E$6:$E$10,"Ambos")</f>
         <v/>
       </c>
     </row>
@@ -11464,19 +11485,19 @@
         <v/>
       </c>
       <c r="D101" s="21">
-        <f>SUMIFS('S1'!$I$6:$I$32,'S1'!$B$6:$B$32,$A101,'S1'!$E$6:$E$32,"Víctor")+SUMIFS('S1'!$I$6:$I$32,'S1'!$B$6:$B$32,$A101,'S1'!$E$6:$E$32,"Ambos")+SUMIFS('S2'!$I$6:$I$23,'S2'!$B$6:$B$23,$A101,'S2'!$E$6:$E$23,"Víctor")+SUMIFS('S2'!$I$6:$I$23,'S2'!$B$6:$B$23,$A101,'S2'!$E$6:$E$23,"Ambos")+SUMIFS('S3'!$I$6:$I$19,'S3'!$B$6:$B$19,$A101,'S3'!$E$6:$E$19,"Víctor")+SUMIFS('S3'!$I$6:$I$19,'S3'!$B$6:$B$19,$A101,'S3'!$E$6:$E$19,"Ambos")+SUMIFS('S4'!$I$6:$I$20,'S4'!$B$6:$B$20,$A101,'S4'!$E$6:$E$20,"Víctor")+SUMIFS('S4'!$I$6:$I$20,'S4'!$B$6:$B$20,$A101,'S4'!$E$6:$E$20,"Ambos")+SUMIFS('S5'!$I$6:$I$20,'S5'!$B$6:$B$20,$A101,'S5'!$E$6:$E$20,"Víctor")+SUMIFS('S5'!$I$6:$I$20,'S5'!$B$6:$B$20,$A101,'S5'!$E$6:$E$20,"Ambos")+SUMIFS('S6'!$I$6:$I$17,'S6'!$B$6:$B$17,$A101,'S6'!$E$6:$E$17,"Víctor")+SUMIFS('S6'!$I$6:$I$17,'S6'!$B$6:$B$17,$A101,'S6'!$E$6:$E$17,"Ambos")+SUMIFS('S7'!$I$6:$I$19,'S7'!$B$6:$B$19,$A101,'S7'!$E$6:$E$19,"Víctor")+SUMIFS('S7'!$I$6:$I$19,'S7'!$B$6:$B$19,$A101,'S7'!$E$6:$E$19,"Ambos")+SUMIFS('S8'!$I$6:$I$23,'S8'!$B$6:$B$23,$A101,'S8'!$E$6:$E$23,"Víctor")+SUMIFS('S8'!$I$6:$I$23,'S8'!$B$6:$B$23,$A101,'S8'!$E$6:$E$23,"Ambos")+SUMIFS('S9'!$I$6:$I$15,'S9'!$B$6:$B$15,$A101,'S9'!$E$6:$E$15,"Víctor")+SUMIFS('S9'!$I$6:$I$15,'S9'!$B$6:$B$15,$A101,'S9'!$E$6:$E$15,"Ambos")+SUMIFS('S10'!$I$6:$I$13,'S10'!$B$6:$B$13,$A101,'S10'!$E$6:$E$13,"Víctor")+SUMIFS('S10'!$I$6:$I$13,'S10'!$B$6:$B$13,$A101,'S10'!$E$6:$E$13,"Ambos")+SUMIFS('Holgura'!$I$6:$I$11,'Holgura'!$B$6:$B$11,$A101,'Holgura'!$E$6:$E$11,"Víctor")+SUMIFS('Holgura'!$I$6:$I$11,'Holgura'!$B$6:$B$11,$A101,'Holgura'!$E$6:$E$11,"Ambos")+SUMIFS('Entrega'!$I$6:$I$9,'Entrega'!$B$6:$B$9,$A101,'Entrega'!$E$6:$E$9,"Víctor")+SUMIFS('Entrega'!$I$6:$I$9,'Entrega'!$B$6:$B$9,$A101,'Entrega'!$E$6:$E$9,"Ambos")+SUMIFS('Defensa'!$I$6:$I$10,'Defensa'!$B$6:$B$10,$A101,'Defensa'!$E$6:$E$10,"Víctor")+SUMIFS('Defensa'!$I$6:$I$10,'Defensa'!$B$6:$B$10,$A101,'Defensa'!$E$6:$E$10,"Ambos")</f>
+        <f>SUMIFS('S1'!$I$6:$I$32,'S1'!$B$6:$B$32,$A101,'S1'!$E$6:$E$32,"Víctor")+SUMIFS('S1'!$I$6:$I$32,'S1'!$B$6:$B$32,$A101,'S1'!$E$6:$E$32,"Ambos")+SUMIFS('S2'!$I$6:$I$23,'S2'!$B$6:$B$23,$A101,'S2'!$E$6:$E$23,"Víctor")+SUMIFS('S2'!$I$6:$I$23,'S2'!$B$6:$B$23,$A101,'S2'!$E$6:$E$23,"Ambos")+SUMIFS('S3'!$I$6:$I$24,'S3'!$B$6:$B$24,$A101,'S3'!$E$6:$E$24,"Víctor")+SUMIFS('S3'!$I$6:$I$24,'S3'!$B$6:$B$24,$A101,'S3'!$E$6:$E$24,"Ambos")+SUMIFS('S4'!$I$6:$I$22,'S4'!$B$6:$B$22,$A101,'S4'!$E$6:$E$22,"Víctor")+SUMIFS('S4'!$I$6:$I$22,'S4'!$B$6:$B$22,$A101,'S4'!$E$6:$E$22,"Ambos")+SUMIFS('S5'!$I$6:$I$20,'S5'!$B$6:$B$20,$A101,'S5'!$E$6:$E$20,"Víctor")+SUMIFS('S5'!$I$6:$I$20,'S5'!$B$6:$B$20,$A101,'S5'!$E$6:$E$20,"Ambos")+SUMIFS('S6'!$I$6:$I$17,'S6'!$B$6:$B$17,$A101,'S6'!$E$6:$E$17,"Víctor")+SUMIFS('S6'!$I$6:$I$17,'S6'!$B$6:$B$17,$A101,'S6'!$E$6:$E$17,"Ambos")+SUMIFS('S7'!$I$6:$I$19,'S7'!$B$6:$B$19,$A101,'S7'!$E$6:$E$19,"Víctor")+SUMIFS('S7'!$I$6:$I$19,'S7'!$B$6:$B$19,$A101,'S7'!$E$6:$E$19,"Ambos")+SUMIFS('S8'!$I$6:$I$23,'S8'!$B$6:$B$23,$A101,'S8'!$E$6:$E$23,"Víctor")+SUMIFS('S8'!$I$6:$I$23,'S8'!$B$6:$B$23,$A101,'S8'!$E$6:$E$23,"Ambos")+SUMIFS('S9'!$I$6:$I$15,'S9'!$B$6:$B$15,$A101,'S9'!$E$6:$E$15,"Víctor")+SUMIFS('S9'!$I$6:$I$15,'S9'!$B$6:$B$15,$A101,'S9'!$E$6:$E$15,"Ambos")+SUMIFS('S10'!$I$6:$I$13,'S10'!$B$6:$B$13,$A101,'S10'!$E$6:$E$13,"Víctor")+SUMIFS('S10'!$I$6:$I$13,'S10'!$B$6:$B$13,$A101,'S10'!$E$6:$E$13,"Ambos")+SUMIFS('Holgura'!$I$6:$I$11,'Holgura'!$B$6:$B$11,$A101,'Holgura'!$E$6:$E$11,"Víctor")+SUMIFS('Holgura'!$I$6:$I$11,'Holgura'!$B$6:$B$11,$A101,'Holgura'!$E$6:$E$11,"Ambos")+SUMIFS('Entrega'!$I$6:$I$9,'Entrega'!$B$6:$B$9,$A101,'Entrega'!$E$6:$E$9,"Víctor")+SUMIFS('Entrega'!$I$6:$I$9,'Entrega'!$B$6:$B$9,$A101,'Entrega'!$E$6:$E$9,"Ambos")+SUMIFS('Defensa'!$I$6:$I$10,'Defensa'!$B$6:$B$10,$A101,'Defensa'!$E$6:$E$10,"Víctor")+SUMIFS('Defensa'!$I$6:$I$10,'Defensa'!$B$6:$B$10,$A101,'Defensa'!$E$6:$E$10,"Ambos")</f>
         <v/>
       </c>
       <c r="E101" s="21">
-        <f>SUMIFS('S1'!$I$6:$I$32,'S1'!$B$6:$B$32,$A101,'S1'!$E$6:$E$32,"Diego")+SUMIFS('S1'!$I$6:$I$32,'S1'!$B$6:$B$32,$A101,'S1'!$E$6:$E$32,"Ambos")+SUMIFS('S2'!$I$6:$I$23,'S2'!$B$6:$B$23,$A101,'S2'!$E$6:$E$23,"Diego")+SUMIFS('S2'!$I$6:$I$23,'S2'!$B$6:$B$23,$A101,'S2'!$E$6:$E$23,"Ambos")+SUMIFS('S3'!$I$6:$I$19,'S3'!$B$6:$B$19,$A101,'S3'!$E$6:$E$19,"Diego")+SUMIFS('S3'!$I$6:$I$19,'S3'!$B$6:$B$19,$A101,'S3'!$E$6:$E$19,"Ambos")+SUMIFS('S4'!$I$6:$I$20,'S4'!$B$6:$B$20,$A101,'S4'!$E$6:$E$20,"Diego")+SUMIFS('S4'!$I$6:$I$20,'S4'!$B$6:$B$20,$A101,'S4'!$E$6:$E$20,"Ambos")+SUMIFS('S5'!$I$6:$I$20,'S5'!$B$6:$B$20,$A101,'S5'!$E$6:$E$20,"Diego")+SUMIFS('S5'!$I$6:$I$20,'S5'!$B$6:$B$20,$A101,'S5'!$E$6:$E$20,"Ambos")+SUMIFS('S6'!$I$6:$I$17,'S6'!$B$6:$B$17,$A101,'S6'!$E$6:$E$17,"Diego")+SUMIFS('S6'!$I$6:$I$17,'S6'!$B$6:$B$17,$A101,'S6'!$E$6:$E$17,"Ambos")+SUMIFS('S7'!$I$6:$I$19,'S7'!$B$6:$B$19,$A101,'S7'!$E$6:$E$19,"Diego")+SUMIFS('S7'!$I$6:$I$19,'S7'!$B$6:$B$19,$A101,'S7'!$E$6:$E$19,"Ambos")+SUMIFS('S8'!$I$6:$I$23,'S8'!$B$6:$B$23,$A101,'S8'!$E$6:$E$23,"Diego")+SUMIFS('S8'!$I$6:$I$23,'S8'!$B$6:$B$23,$A101,'S8'!$E$6:$E$23,"Ambos")+SUMIFS('S9'!$I$6:$I$15,'S9'!$B$6:$B$15,$A101,'S9'!$E$6:$E$15,"Diego")+SUMIFS('S9'!$I$6:$I$15,'S9'!$B$6:$B$15,$A101,'S9'!$E$6:$E$15,"Ambos")+SUMIFS('S10'!$I$6:$I$13,'S10'!$B$6:$B$13,$A101,'S10'!$E$6:$E$13,"Diego")+SUMIFS('S10'!$I$6:$I$13,'S10'!$B$6:$B$13,$A101,'S10'!$E$6:$E$13,"Ambos")+SUMIFS('Holgura'!$I$6:$I$11,'Holgura'!$B$6:$B$11,$A101,'Holgura'!$E$6:$E$11,"Diego")+SUMIFS('Holgura'!$I$6:$I$11,'Holgura'!$B$6:$B$11,$A101,'Holgura'!$E$6:$E$11,"Ambos")+SUMIFS('Entrega'!$I$6:$I$9,'Entrega'!$B$6:$B$9,$A101,'Entrega'!$E$6:$E$9,"Diego")+SUMIFS('Entrega'!$I$6:$I$9,'Entrega'!$B$6:$B$9,$A101,'Entrega'!$E$6:$E$9,"Ambos")+SUMIFS('Defensa'!$I$6:$I$10,'Defensa'!$B$6:$B$10,$A101,'Defensa'!$E$6:$E$10,"Diego")+SUMIFS('Defensa'!$I$6:$I$10,'Defensa'!$B$6:$B$10,$A101,'Defensa'!$E$6:$E$10,"Ambos")</f>
+        <f>SUMIFS('S1'!$I$6:$I$32,'S1'!$B$6:$B$32,$A101,'S1'!$E$6:$E$32,"Diego")+SUMIFS('S1'!$I$6:$I$32,'S1'!$B$6:$B$32,$A101,'S1'!$E$6:$E$32,"Ambos")+SUMIFS('S2'!$I$6:$I$23,'S2'!$B$6:$B$23,$A101,'S2'!$E$6:$E$23,"Diego")+SUMIFS('S2'!$I$6:$I$23,'S2'!$B$6:$B$23,$A101,'S2'!$E$6:$E$23,"Ambos")+SUMIFS('S3'!$I$6:$I$24,'S3'!$B$6:$B$24,$A101,'S3'!$E$6:$E$24,"Diego")+SUMIFS('S3'!$I$6:$I$24,'S3'!$B$6:$B$24,$A101,'S3'!$E$6:$E$24,"Ambos")+SUMIFS('S4'!$I$6:$I$22,'S4'!$B$6:$B$22,$A101,'S4'!$E$6:$E$22,"Diego")+SUMIFS('S4'!$I$6:$I$22,'S4'!$B$6:$B$22,$A101,'S4'!$E$6:$E$22,"Ambos")+SUMIFS('S5'!$I$6:$I$20,'S5'!$B$6:$B$20,$A101,'S5'!$E$6:$E$20,"Diego")+SUMIFS('S5'!$I$6:$I$20,'S5'!$B$6:$B$20,$A101,'S5'!$E$6:$E$20,"Ambos")+SUMIFS('S6'!$I$6:$I$17,'S6'!$B$6:$B$17,$A101,'S6'!$E$6:$E$17,"Diego")+SUMIFS('S6'!$I$6:$I$17,'S6'!$B$6:$B$17,$A101,'S6'!$E$6:$E$17,"Ambos")+SUMIFS('S7'!$I$6:$I$19,'S7'!$B$6:$B$19,$A101,'S7'!$E$6:$E$19,"Diego")+SUMIFS('S7'!$I$6:$I$19,'S7'!$B$6:$B$19,$A101,'S7'!$E$6:$E$19,"Ambos")+SUMIFS('S8'!$I$6:$I$23,'S8'!$B$6:$B$23,$A101,'S8'!$E$6:$E$23,"Diego")+SUMIFS('S8'!$I$6:$I$23,'S8'!$B$6:$B$23,$A101,'S8'!$E$6:$E$23,"Ambos")+SUMIFS('S9'!$I$6:$I$15,'S9'!$B$6:$B$15,$A101,'S9'!$E$6:$E$15,"Diego")+SUMIFS('S9'!$I$6:$I$15,'S9'!$B$6:$B$15,$A101,'S9'!$E$6:$E$15,"Ambos")+SUMIFS('S10'!$I$6:$I$13,'S10'!$B$6:$B$13,$A101,'S10'!$E$6:$E$13,"Diego")+SUMIFS('S10'!$I$6:$I$13,'S10'!$B$6:$B$13,$A101,'S10'!$E$6:$E$13,"Ambos")+SUMIFS('Holgura'!$I$6:$I$11,'Holgura'!$B$6:$B$11,$A101,'Holgura'!$E$6:$E$11,"Diego")+SUMIFS('Holgura'!$I$6:$I$11,'Holgura'!$B$6:$B$11,$A101,'Holgura'!$E$6:$E$11,"Ambos")+SUMIFS('Entrega'!$I$6:$I$9,'Entrega'!$B$6:$B$9,$A101,'Entrega'!$E$6:$E$9,"Diego")+SUMIFS('Entrega'!$I$6:$I$9,'Entrega'!$B$6:$B$9,$A101,'Entrega'!$E$6:$E$9,"Ambos")+SUMIFS('Defensa'!$I$6:$I$10,'Defensa'!$B$6:$B$10,$A101,'Defensa'!$E$6:$E$10,"Diego")+SUMIFS('Defensa'!$I$6:$I$10,'Defensa'!$B$6:$B$10,$A101,'Defensa'!$E$6:$E$10,"Ambos")</f>
         <v/>
       </c>
       <c r="F101" s="21">
-        <f>COUNTIFS('S1'!$B$6:$B$32,$A101,'S1'!$E$6:$E$32,"Víctor")+COUNTIFS('S1'!$B$6:$B$32,$A101,'S1'!$E$6:$E$32,"Ambos")+COUNTIFS('S2'!$B$6:$B$23,$A101,'S2'!$E$6:$E$23,"Víctor")+COUNTIFS('S2'!$B$6:$B$23,$A101,'S2'!$E$6:$E$23,"Ambos")+COUNTIFS('S3'!$B$6:$B$19,$A101,'S3'!$E$6:$E$19,"Víctor")+COUNTIFS('S3'!$B$6:$B$19,$A101,'S3'!$E$6:$E$19,"Ambos")+COUNTIFS('S4'!$B$6:$B$20,$A101,'S4'!$E$6:$E$20,"Víctor")+COUNTIFS('S4'!$B$6:$B$20,$A101,'S4'!$E$6:$E$20,"Ambos")+COUNTIFS('S5'!$B$6:$B$20,$A101,'S5'!$E$6:$E$20,"Víctor")+COUNTIFS('S5'!$B$6:$B$20,$A101,'S5'!$E$6:$E$20,"Ambos")+COUNTIFS('S6'!$B$6:$B$17,$A101,'S6'!$E$6:$E$17,"Víctor")+COUNTIFS('S6'!$B$6:$B$17,$A101,'S6'!$E$6:$E$17,"Ambos")+COUNTIFS('S7'!$B$6:$B$19,$A101,'S7'!$E$6:$E$19,"Víctor")+COUNTIFS('S7'!$B$6:$B$19,$A101,'S7'!$E$6:$E$19,"Ambos")+COUNTIFS('S8'!$B$6:$B$23,$A101,'S8'!$E$6:$E$23,"Víctor")+COUNTIFS('S8'!$B$6:$B$23,$A101,'S8'!$E$6:$E$23,"Ambos")+COUNTIFS('S9'!$B$6:$B$15,$A101,'S9'!$E$6:$E$15,"Víctor")+COUNTIFS('S9'!$B$6:$B$15,$A101,'S9'!$E$6:$E$15,"Ambos")+COUNTIFS('S10'!$B$6:$B$13,$A101,'S10'!$E$6:$E$13,"Víctor")+COUNTIFS('S10'!$B$6:$B$13,$A101,'S10'!$E$6:$E$13,"Ambos")+COUNTIFS('Holgura'!$B$6:$B$11,$A101,'Holgura'!$E$6:$E$11,"Víctor")+COUNTIFS('Holgura'!$B$6:$B$11,$A101,'Holgura'!$E$6:$E$11,"Ambos")+COUNTIFS('Entrega'!$B$6:$B$9,$A101,'Entrega'!$E$6:$E$9,"Víctor")+COUNTIFS('Entrega'!$B$6:$B$9,$A101,'Entrega'!$E$6:$E$9,"Ambos")+COUNTIFS('Defensa'!$B$6:$B$10,$A101,'Defensa'!$E$6:$E$10,"Víctor")+COUNTIFS('Defensa'!$B$6:$B$10,$A101,'Defensa'!$E$6:$E$10,"Ambos")</f>
+        <f>COUNTIFS('S1'!$B$6:$B$32,$A101,'S1'!$E$6:$E$32,"Víctor")+COUNTIFS('S1'!$B$6:$B$32,$A101,'S1'!$E$6:$E$32,"Ambos")+COUNTIFS('S2'!$B$6:$B$23,$A101,'S2'!$E$6:$E$23,"Víctor")+COUNTIFS('S2'!$B$6:$B$23,$A101,'S2'!$E$6:$E$23,"Ambos")+COUNTIFS('S3'!$B$6:$B$24,$A101,'S3'!$E$6:$E$24,"Víctor")+COUNTIFS('S3'!$B$6:$B$24,$A101,'S3'!$E$6:$E$24,"Ambos")+COUNTIFS('S4'!$B$6:$B$22,$A101,'S4'!$E$6:$E$22,"Víctor")+COUNTIFS('S4'!$B$6:$B$22,$A101,'S4'!$E$6:$E$22,"Ambos")+COUNTIFS('S5'!$B$6:$B$20,$A101,'S5'!$E$6:$E$20,"Víctor")+COUNTIFS('S5'!$B$6:$B$20,$A101,'S5'!$E$6:$E$20,"Ambos")+COUNTIFS('S6'!$B$6:$B$17,$A101,'S6'!$E$6:$E$17,"Víctor")+COUNTIFS('S6'!$B$6:$B$17,$A101,'S6'!$E$6:$E$17,"Ambos")+COUNTIFS('S7'!$B$6:$B$19,$A101,'S7'!$E$6:$E$19,"Víctor")+COUNTIFS('S7'!$B$6:$B$19,$A101,'S7'!$E$6:$E$19,"Ambos")+COUNTIFS('S8'!$B$6:$B$23,$A101,'S8'!$E$6:$E$23,"Víctor")+COUNTIFS('S8'!$B$6:$B$23,$A101,'S8'!$E$6:$E$23,"Ambos")+COUNTIFS('S9'!$B$6:$B$15,$A101,'S9'!$E$6:$E$15,"Víctor")+COUNTIFS('S9'!$B$6:$B$15,$A101,'S9'!$E$6:$E$15,"Ambos")+COUNTIFS('S10'!$B$6:$B$13,$A101,'S10'!$E$6:$E$13,"Víctor")+COUNTIFS('S10'!$B$6:$B$13,$A101,'S10'!$E$6:$E$13,"Ambos")+COUNTIFS('Holgura'!$B$6:$B$11,$A101,'Holgura'!$E$6:$E$11,"Víctor")+COUNTIFS('Holgura'!$B$6:$B$11,$A101,'Holgura'!$E$6:$E$11,"Ambos")+COUNTIFS('Entrega'!$B$6:$B$9,$A101,'Entrega'!$E$6:$E$9,"Víctor")+COUNTIFS('Entrega'!$B$6:$B$9,$A101,'Entrega'!$E$6:$E$9,"Ambos")+COUNTIFS('Defensa'!$B$6:$B$10,$A101,'Defensa'!$E$6:$E$10,"Víctor")+COUNTIFS('Defensa'!$B$6:$B$10,$A101,'Defensa'!$E$6:$E$10,"Ambos")</f>
         <v/>
       </c>
       <c r="G101" s="21">
-        <f>COUNTIFS('S1'!$B$6:$B$32,$A101,'S1'!$E$6:$E$32,"Diego")+COUNTIFS('S1'!$B$6:$B$32,$A101,'S1'!$E$6:$E$32,"Ambos")+COUNTIFS('S2'!$B$6:$B$23,$A101,'S2'!$E$6:$E$23,"Diego")+COUNTIFS('S2'!$B$6:$B$23,$A101,'S2'!$E$6:$E$23,"Ambos")+COUNTIFS('S3'!$B$6:$B$19,$A101,'S3'!$E$6:$E$19,"Diego")+COUNTIFS('S3'!$B$6:$B$19,$A101,'S3'!$E$6:$E$19,"Ambos")+COUNTIFS('S4'!$B$6:$B$20,$A101,'S4'!$E$6:$E$20,"Diego")+COUNTIFS('S4'!$B$6:$B$20,$A101,'S4'!$E$6:$E$20,"Ambos")+COUNTIFS('S5'!$B$6:$B$20,$A101,'S5'!$E$6:$E$20,"Diego")+COUNTIFS('S5'!$B$6:$B$20,$A101,'S5'!$E$6:$E$20,"Ambos")+COUNTIFS('S6'!$B$6:$B$17,$A101,'S6'!$E$6:$E$17,"Diego")+COUNTIFS('S6'!$B$6:$B$17,$A101,'S6'!$E$6:$E$17,"Ambos")+COUNTIFS('S7'!$B$6:$B$19,$A101,'S7'!$E$6:$E$19,"Diego")+COUNTIFS('S7'!$B$6:$B$19,$A101,'S7'!$E$6:$E$19,"Ambos")+COUNTIFS('S8'!$B$6:$B$23,$A101,'S8'!$E$6:$E$23,"Diego")+COUNTIFS('S8'!$B$6:$B$23,$A101,'S8'!$E$6:$E$23,"Ambos")+COUNTIFS('S9'!$B$6:$B$15,$A101,'S9'!$E$6:$E$15,"Diego")+COUNTIFS('S9'!$B$6:$B$15,$A101,'S9'!$E$6:$E$15,"Ambos")+COUNTIFS('S10'!$B$6:$B$13,$A101,'S10'!$E$6:$E$13,"Diego")+COUNTIFS('S10'!$B$6:$B$13,$A101,'S10'!$E$6:$E$13,"Ambos")+COUNTIFS('Holgura'!$B$6:$B$11,$A101,'Holgura'!$E$6:$E$11,"Diego")+COUNTIFS('Holgura'!$B$6:$B$11,$A101,'Holgura'!$E$6:$E$11,"Ambos")+COUNTIFS('Entrega'!$B$6:$B$9,$A101,'Entrega'!$E$6:$E$9,"Diego")+COUNTIFS('Entrega'!$B$6:$B$9,$A101,'Entrega'!$E$6:$E$9,"Ambos")+COUNTIFS('Defensa'!$B$6:$B$10,$A101,'Defensa'!$E$6:$E$10,"Diego")+COUNTIFS('Defensa'!$B$6:$B$10,$A101,'Defensa'!$E$6:$E$10,"Ambos")</f>
+        <f>COUNTIFS('S1'!$B$6:$B$32,$A101,'S1'!$E$6:$E$32,"Diego")+COUNTIFS('S1'!$B$6:$B$32,$A101,'S1'!$E$6:$E$32,"Ambos")+COUNTIFS('S2'!$B$6:$B$23,$A101,'S2'!$E$6:$E$23,"Diego")+COUNTIFS('S2'!$B$6:$B$23,$A101,'S2'!$E$6:$E$23,"Ambos")+COUNTIFS('S3'!$B$6:$B$24,$A101,'S3'!$E$6:$E$24,"Diego")+COUNTIFS('S3'!$B$6:$B$24,$A101,'S3'!$E$6:$E$24,"Ambos")+COUNTIFS('S4'!$B$6:$B$22,$A101,'S4'!$E$6:$E$22,"Diego")+COUNTIFS('S4'!$B$6:$B$22,$A101,'S4'!$E$6:$E$22,"Ambos")+COUNTIFS('S5'!$B$6:$B$20,$A101,'S5'!$E$6:$E$20,"Diego")+COUNTIFS('S5'!$B$6:$B$20,$A101,'S5'!$E$6:$E$20,"Ambos")+COUNTIFS('S6'!$B$6:$B$17,$A101,'S6'!$E$6:$E$17,"Diego")+COUNTIFS('S6'!$B$6:$B$17,$A101,'S6'!$E$6:$E$17,"Ambos")+COUNTIFS('S7'!$B$6:$B$19,$A101,'S7'!$E$6:$E$19,"Diego")+COUNTIFS('S7'!$B$6:$B$19,$A101,'S7'!$E$6:$E$19,"Ambos")+COUNTIFS('S8'!$B$6:$B$23,$A101,'S8'!$E$6:$E$23,"Diego")+COUNTIFS('S8'!$B$6:$B$23,$A101,'S8'!$E$6:$E$23,"Ambos")+COUNTIFS('S9'!$B$6:$B$15,$A101,'S9'!$E$6:$E$15,"Diego")+COUNTIFS('S9'!$B$6:$B$15,$A101,'S9'!$E$6:$E$15,"Ambos")+COUNTIFS('S10'!$B$6:$B$13,$A101,'S10'!$E$6:$E$13,"Diego")+COUNTIFS('S10'!$B$6:$B$13,$A101,'S10'!$E$6:$E$13,"Ambos")+COUNTIFS('Holgura'!$B$6:$B$11,$A101,'Holgura'!$E$6:$E$11,"Diego")+COUNTIFS('Holgura'!$B$6:$B$11,$A101,'Holgura'!$E$6:$E$11,"Ambos")+COUNTIFS('Entrega'!$B$6:$B$9,$A101,'Entrega'!$E$6:$E$9,"Diego")+COUNTIFS('Entrega'!$B$6:$B$9,$A101,'Entrega'!$E$6:$E$9,"Ambos")+COUNTIFS('Defensa'!$B$6:$B$10,$A101,'Defensa'!$E$6:$E$10,"Diego")+COUNTIFS('Defensa'!$B$6:$B$10,$A101,'Defensa'!$E$6:$E$10,"Ambos")</f>
         <v/>
       </c>
     </row>
@@ -11493,19 +11514,19 @@
         <v/>
       </c>
       <c r="D102" s="21">
-        <f>SUMIFS('S1'!$I$6:$I$32,'S1'!$B$6:$B$32,$A102,'S1'!$E$6:$E$32,"Víctor")+SUMIFS('S1'!$I$6:$I$32,'S1'!$B$6:$B$32,$A102,'S1'!$E$6:$E$32,"Ambos")+SUMIFS('S2'!$I$6:$I$23,'S2'!$B$6:$B$23,$A102,'S2'!$E$6:$E$23,"Víctor")+SUMIFS('S2'!$I$6:$I$23,'S2'!$B$6:$B$23,$A102,'S2'!$E$6:$E$23,"Ambos")+SUMIFS('S3'!$I$6:$I$19,'S3'!$B$6:$B$19,$A102,'S3'!$E$6:$E$19,"Víctor")+SUMIFS('S3'!$I$6:$I$19,'S3'!$B$6:$B$19,$A102,'S3'!$E$6:$E$19,"Ambos")+SUMIFS('S4'!$I$6:$I$20,'S4'!$B$6:$B$20,$A102,'S4'!$E$6:$E$20,"Víctor")+SUMIFS('S4'!$I$6:$I$20,'S4'!$B$6:$B$20,$A102,'S4'!$E$6:$E$20,"Ambos")+SUMIFS('S5'!$I$6:$I$20,'S5'!$B$6:$B$20,$A102,'S5'!$E$6:$E$20,"Víctor")+SUMIFS('S5'!$I$6:$I$20,'S5'!$B$6:$B$20,$A102,'S5'!$E$6:$E$20,"Ambos")+SUMIFS('S6'!$I$6:$I$17,'S6'!$B$6:$B$17,$A102,'S6'!$E$6:$E$17,"Víctor")+SUMIFS('S6'!$I$6:$I$17,'S6'!$B$6:$B$17,$A102,'S6'!$E$6:$E$17,"Ambos")+SUMIFS('S7'!$I$6:$I$19,'S7'!$B$6:$B$19,$A102,'S7'!$E$6:$E$19,"Víctor")+SUMIFS('S7'!$I$6:$I$19,'S7'!$B$6:$B$19,$A102,'S7'!$E$6:$E$19,"Ambos")+SUMIFS('S8'!$I$6:$I$23,'S8'!$B$6:$B$23,$A102,'S8'!$E$6:$E$23,"Víctor")+SUMIFS('S8'!$I$6:$I$23,'S8'!$B$6:$B$23,$A102,'S8'!$E$6:$E$23,"Ambos")+SUMIFS('S9'!$I$6:$I$15,'S9'!$B$6:$B$15,$A102,'S9'!$E$6:$E$15,"Víctor")+SUMIFS('S9'!$I$6:$I$15,'S9'!$B$6:$B$15,$A102,'S9'!$E$6:$E$15,"Ambos")+SUMIFS('S10'!$I$6:$I$13,'S10'!$B$6:$B$13,$A102,'S10'!$E$6:$E$13,"Víctor")+SUMIFS('S10'!$I$6:$I$13,'S10'!$B$6:$B$13,$A102,'S10'!$E$6:$E$13,"Ambos")+SUMIFS('Holgura'!$I$6:$I$11,'Holgura'!$B$6:$B$11,$A102,'Holgura'!$E$6:$E$11,"Víctor")+SUMIFS('Holgura'!$I$6:$I$11,'Holgura'!$B$6:$B$11,$A102,'Holgura'!$E$6:$E$11,"Ambos")+SUMIFS('Entrega'!$I$6:$I$9,'Entrega'!$B$6:$B$9,$A102,'Entrega'!$E$6:$E$9,"Víctor")+SUMIFS('Entrega'!$I$6:$I$9,'Entrega'!$B$6:$B$9,$A102,'Entrega'!$E$6:$E$9,"Ambos")+SUMIFS('Defensa'!$I$6:$I$10,'Defensa'!$B$6:$B$10,$A102,'Defensa'!$E$6:$E$10,"Víctor")+SUMIFS('Defensa'!$I$6:$I$10,'Defensa'!$B$6:$B$10,$A102,'Defensa'!$E$6:$E$10,"Ambos")</f>
+        <f>SUMIFS('S1'!$I$6:$I$32,'S1'!$B$6:$B$32,$A102,'S1'!$E$6:$E$32,"Víctor")+SUMIFS('S1'!$I$6:$I$32,'S1'!$B$6:$B$32,$A102,'S1'!$E$6:$E$32,"Ambos")+SUMIFS('S2'!$I$6:$I$23,'S2'!$B$6:$B$23,$A102,'S2'!$E$6:$E$23,"Víctor")+SUMIFS('S2'!$I$6:$I$23,'S2'!$B$6:$B$23,$A102,'S2'!$E$6:$E$23,"Ambos")+SUMIFS('S3'!$I$6:$I$24,'S3'!$B$6:$B$24,$A102,'S3'!$E$6:$E$24,"Víctor")+SUMIFS('S3'!$I$6:$I$24,'S3'!$B$6:$B$24,$A102,'S3'!$E$6:$E$24,"Ambos")+SUMIFS('S4'!$I$6:$I$22,'S4'!$B$6:$B$22,$A102,'S4'!$E$6:$E$22,"Víctor")+SUMIFS('S4'!$I$6:$I$22,'S4'!$B$6:$B$22,$A102,'S4'!$E$6:$E$22,"Ambos")+SUMIFS('S5'!$I$6:$I$20,'S5'!$B$6:$B$20,$A102,'S5'!$E$6:$E$20,"Víctor")+SUMIFS('S5'!$I$6:$I$20,'S5'!$B$6:$B$20,$A102,'S5'!$E$6:$E$20,"Ambos")+SUMIFS('S6'!$I$6:$I$17,'S6'!$B$6:$B$17,$A102,'S6'!$E$6:$E$17,"Víctor")+SUMIFS('S6'!$I$6:$I$17,'S6'!$B$6:$B$17,$A102,'S6'!$E$6:$E$17,"Ambos")+SUMIFS('S7'!$I$6:$I$19,'S7'!$B$6:$B$19,$A102,'S7'!$E$6:$E$19,"Víctor")+SUMIFS('S7'!$I$6:$I$19,'S7'!$B$6:$B$19,$A102,'S7'!$E$6:$E$19,"Ambos")+SUMIFS('S8'!$I$6:$I$23,'S8'!$B$6:$B$23,$A102,'S8'!$E$6:$E$23,"Víctor")+SUMIFS('S8'!$I$6:$I$23,'S8'!$B$6:$B$23,$A102,'S8'!$E$6:$E$23,"Ambos")+SUMIFS('S9'!$I$6:$I$15,'S9'!$B$6:$B$15,$A102,'S9'!$E$6:$E$15,"Víctor")+SUMIFS('S9'!$I$6:$I$15,'S9'!$B$6:$B$15,$A102,'S9'!$E$6:$E$15,"Ambos")+SUMIFS('S10'!$I$6:$I$13,'S10'!$B$6:$B$13,$A102,'S10'!$E$6:$E$13,"Víctor")+SUMIFS('S10'!$I$6:$I$13,'S10'!$B$6:$B$13,$A102,'S10'!$E$6:$E$13,"Ambos")+SUMIFS('Holgura'!$I$6:$I$11,'Holgura'!$B$6:$B$11,$A102,'Holgura'!$E$6:$E$11,"Víctor")+SUMIFS('Holgura'!$I$6:$I$11,'Holgura'!$B$6:$B$11,$A102,'Holgura'!$E$6:$E$11,"Ambos")+SUMIFS('Entrega'!$I$6:$I$9,'Entrega'!$B$6:$B$9,$A102,'Entrega'!$E$6:$E$9,"Víctor")+SUMIFS('Entrega'!$I$6:$I$9,'Entrega'!$B$6:$B$9,$A102,'Entrega'!$E$6:$E$9,"Ambos")+SUMIFS('Defensa'!$I$6:$I$10,'Defensa'!$B$6:$B$10,$A102,'Defensa'!$E$6:$E$10,"Víctor")+SUMIFS('Defensa'!$I$6:$I$10,'Defensa'!$B$6:$B$10,$A102,'Defensa'!$E$6:$E$10,"Ambos")</f>
         <v/>
       </c>
       <c r="E102" s="21">
-        <f>SUMIFS('S1'!$I$6:$I$32,'S1'!$B$6:$B$32,$A102,'S1'!$E$6:$E$32,"Diego")+SUMIFS('S1'!$I$6:$I$32,'S1'!$B$6:$B$32,$A102,'S1'!$E$6:$E$32,"Ambos")+SUMIFS('S2'!$I$6:$I$23,'S2'!$B$6:$B$23,$A102,'S2'!$E$6:$E$23,"Diego")+SUMIFS('S2'!$I$6:$I$23,'S2'!$B$6:$B$23,$A102,'S2'!$E$6:$E$23,"Ambos")+SUMIFS('S3'!$I$6:$I$19,'S3'!$B$6:$B$19,$A102,'S3'!$E$6:$E$19,"Diego")+SUMIFS('S3'!$I$6:$I$19,'S3'!$B$6:$B$19,$A102,'S3'!$E$6:$E$19,"Ambos")+SUMIFS('S4'!$I$6:$I$20,'S4'!$B$6:$B$20,$A102,'S4'!$E$6:$E$20,"Diego")+SUMIFS('S4'!$I$6:$I$20,'S4'!$B$6:$B$20,$A102,'S4'!$E$6:$E$20,"Ambos")+SUMIFS('S5'!$I$6:$I$20,'S5'!$B$6:$B$20,$A102,'S5'!$E$6:$E$20,"Diego")+SUMIFS('S5'!$I$6:$I$20,'S5'!$B$6:$B$20,$A102,'S5'!$E$6:$E$20,"Ambos")+SUMIFS('S6'!$I$6:$I$17,'S6'!$B$6:$B$17,$A102,'S6'!$E$6:$E$17,"Diego")+SUMIFS('S6'!$I$6:$I$17,'S6'!$B$6:$B$17,$A102,'S6'!$E$6:$E$17,"Ambos")+SUMIFS('S7'!$I$6:$I$19,'S7'!$B$6:$B$19,$A102,'S7'!$E$6:$E$19,"Diego")+SUMIFS('S7'!$I$6:$I$19,'S7'!$B$6:$B$19,$A102,'S7'!$E$6:$E$19,"Ambos")+SUMIFS('S8'!$I$6:$I$23,'S8'!$B$6:$B$23,$A102,'S8'!$E$6:$E$23,"Diego")+SUMIFS('S8'!$I$6:$I$23,'S8'!$B$6:$B$23,$A102,'S8'!$E$6:$E$23,"Ambos")+SUMIFS('S9'!$I$6:$I$15,'S9'!$B$6:$B$15,$A102,'S9'!$E$6:$E$15,"Diego")+SUMIFS('S9'!$I$6:$I$15,'S9'!$B$6:$B$15,$A102,'S9'!$E$6:$E$15,"Ambos")+SUMIFS('S10'!$I$6:$I$13,'S10'!$B$6:$B$13,$A102,'S10'!$E$6:$E$13,"Diego")+SUMIFS('S10'!$I$6:$I$13,'S10'!$B$6:$B$13,$A102,'S10'!$E$6:$E$13,"Ambos")+SUMIFS('Holgura'!$I$6:$I$11,'Holgura'!$B$6:$B$11,$A102,'Holgura'!$E$6:$E$11,"Diego")+SUMIFS('Holgura'!$I$6:$I$11,'Holgura'!$B$6:$B$11,$A102,'Holgura'!$E$6:$E$11,"Ambos")+SUMIFS('Entrega'!$I$6:$I$9,'Entrega'!$B$6:$B$9,$A102,'Entrega'!$E$6:$E$9,"Diego")+SUMIFS('Entrega'!$I$6:$I$9,'Entrega'!$B$6:$B$9,$A102,'Entrega'!$E$6:$E$9,"Ambos")+SUMIFS('Defensa'!$I$6:$I$10,'Defensa'!$B$6:$B$10,$A102,'Defensa'!$E$6:$E$10,"Diego")+SUMIFS('Defensa'!$I$6:$I$10,'Defensa'!$B$6:$B$10,$A102,'Defensa'!$E$6:$E$10,"Ambos")</f>
+        <f>SUMIFS('S1'!$I$6:$I$32,'S1'!$B$6:$B$32,$A102,'S1'!$E$6:$E$32,"Diego")+SUMIFS('S1'!$I$6:$I$32,'S1'!$B$6:$B$32,$A102,'S1'!$E$6:$E$32,"Ambos")+SUMIFS('S2'!$I$6:$I$23,'S2'!$B$6:$B$23,$A102,'S2'!$E$6:$E$23,"Diego")+SUMIFS('S2'!$I$6:$I$23,'S2'!$B$6:$B$23,$A102,'S2'!$E$6:$E$23,"Ambos")+SUMIFS('S3'!$I$6:$I$24,'S3'!$B$6:$B$24,$A102,'S3'!$E$6:$E$24,"Diego")+SUMIFS('S3'!$I$6:$I$24,'S3'!$B$6:$B$24,$A102,'S3'!$E$6:$E$24,"Ambos")+SUMIFS('S4'!$I$6:$I$22,'S4'!$B$6:$B$22,$A102,'S4'!$E$6:$E$22,"Diego")+SUMIFS('S4'!$I$6:$I$22,'S4'!$B$6:$B$22,$A102,'S4'!$E$6:$E$22,"Ambos")+SUMIFS('S5'!$I$6:$I$20,'S5'!$B$6:$B$20,$A102,'S5'!$E$6:$E$20,"Diego")+SUMIFS('S5'!$I$6:$I$20,'S5'!$B$6:$B$20,$A102,'S5'!$E$6:$E$20,"Ambos")+SUMIFS('S6'!$I$6:$I$17,'S6'!$B$6:$B$17,$A102,'S6'!$E$6:$E$17,"Diego")+SUMIFS('S6'!$I$6:$I$17,'S6'!$B$6:$B$17,$A102,'S6'!$E$6:$E$17,"Ambos")+SUMIFS('S7'!$I$6:$I$19,'S7'!$B$6:$B$19,$A102,'S7'!$E$6:$E$19,"Diego")+SUMIFS('S7'!$I$6:$I$19,'S7'!$B$6:$B$19,$A102,'S7'!$E$6:$E$19,"Ambos")+SUMIFS('S8'!$I$6:$I$23,'S8'!$B$6:$B$23,$A102,'S8'!$E$6:$E$23,"Diego")+SUMIFS('S8'!$I$6:$I$23,'S8'!$B$6:$B$23,$A102,'S8'!$E$6:$E$23,"Ambos")+SUMIFS('S9'!$I$6:$I$15,'S9'!$B$6:$B$15,$A102,'S9'!$E$6:$E$15,"Diego")+SUMIFS('S9'!$I$6:$I$15,'S9'!$B$6:$B$15,$A102,'S9'!$E$6:$E$15,"Ambos")+SUMIFS('S10'!$I$6:$I$13,'S10'!$B$6:$B$13,$A102,'S10'!$E$6:$E$13,"Diego")+SUMIFS('S10'!$I$6:$I$13,'S10'!$B$6:$B$13,$A102,'S10'!$E$6:$E$13,"Ambos")+SUMIFS('Holgura'!$I$6:$I$11,'Holgura'!$B$6:$B$11,$A102,'Holgura'!$E$6:$E$11,"Diego")+SUMIFS('Holgura'!$I$6:$I$11,'Holgura'!$B$6:$B$11,$A102,'Holgura'!$E$6:$E$11,"Ambos")+SUMIFS('Entrega'!$I$6:$I$9,'Entrega'!$B$6:$B$9,$A102,'Entrega'!$E$6:$E$9,"Diego")+SUMIFS('Entrega'!$I$6:$I$9,'Entrega'!$B$6:$B$9,$A102,'Entrega'!$E$6:$E$9,"Ambos")+SUMIFS('Defensa'!$I$6:$I$10,'Defensa'!$B$6:$B$10,$A102,'Defensa'!$E$6:$E$10,"Diego")+SUMIFS('Defensa'!$I$6:$I$10,'Defensa'!$B$6:$B$10,$A102,'Defensa'!$E$6:$E$10,"Ambos")</f>
         <v/>
       </c>
       <c r="F102" s="21">
-        <f>COUNTIFS('S1'!$B$6:$B$32,$A102,'S1'!$E$6:$E$32,"Víctor")+COUNTIFS('S1'!$B$6:$B$32,$A102,'S1'!$E$6:$E$32,"Ambos")+COUNTIFS('S2'!$B$6:$B$23,$A102,'S2'!$E$6:$E$23,"Víctor")+COUNTIFS('S2'!$B$6:$B$23,$A102,'S2'!$E$6:$E$23,"Ambos")+COUNTIFS('S3'!$B$6:$B$19,$A102,'S3'!$E$6:$E$19,"Víctor")+COUNTIFS('S3'!$B$6:$B$19,$A102,'S3'!$E$6:$E$19,"Ambos")+COUNTIFS('S4'!$B$6:$B$20,$A102,'S4'!$E$6:$E$20,"Víctor")+COUNTIFS('S4'!$B$6:$B$20,$A102,'S4'!$E$6:$E$20,"Ambos")+COUNTIFS('S5'!$B$6:$B$20,$A102,'S5'!$E$6:$E$20,"Víctor")+COUNTIFS('S5'!$B$6:$B$20,$A102,'S5'!$E$6:$E$20,"Ambos")+COUNTIFS('S6'!$B$6:$B$17,$A102,'S6'!$E$6:$E$17,"Víctor")+COUNTIFS('S6'!$B$6:$B$17,$A102,'S6'!$E$6:$E$17,"Ambos")+COUNTIFS('S7'!$B$6:$B$19,$A102,'S7'!$E$6:$E$19,"Víctor")+COUNTIFS('S7'!$B$6:$B$19,$A102,'S7'!$E$6:$E$19,"Ambos")+COUNTIFS('S8'!$B$6:$B$23,$A102,'S8'!$E$6:$E$23,"Víctor")+COUNTIFS('S8'!$B$6:$B$23,$A102,'S8'!$E$6:$E$23,"Ambos")+COUNTIFS('S9'!$B$6:$B$15,$A102,'S9'!$E$6:$E$15,"Víctor")+COUNTIFS('S9'!$B$6:$B$15,$A102,'S9'!$E$6:$E$15,"Ambos")+COUNTIFS('S10'!$B$6:$B$13,$A102,'S10'!$E$6:$E$13,"Víctor")+COUNTIFS('S10'!$B$6:$B$13,$A102,'S10'!$E$6:$E$13,"Ambos")+COUNTIFS('Holgura'!$B$6:$B$11,$A102,'Holgura'!$E$6:$E$11,"Víctor")+COUNTIFS('Holgura'!$B$6:$B$11,$A102,'Holgura'!$E$6:$E$11,"Ambos")+COUNTIFS('Entrega'!$B$6:$B$9,$A102,'Entrega'!$E$6:$E$9,"Víctor")+COUNTIFS('Entrega'!$B$6:$B$9,$A102,'Entrega'!$E$6:$E$9,"Ambos")+COUNTIFS('Defensa'!$B$6:$B$10,$A102,'Defensa'!$E$6:$E$10,"Víctor")+COUNTIFS('Defensa'!$B$6:$B$10,$A102,'Defensa'!$E$6:$E$10,"Ambos")</f>
+        <f>COUNTIFS('S1'!$B$6:$B$32,$A102,'S1'!$E$6:$E$32,"Víctor")+COUNTIFS('S1'!$B$6:$B$32,$A102,'S1'!$E$6:$E$32,"Ambos")+COUNTIFS('S2'!$B$6:$B$23,$A102,'S2'!$E$6:$E$23,"Víctor")+COUNTIFS('S2'!$B$6:$B$23,$A102,'S2'!$E$6:$E$23,"Ambos")+COUNTIFS('S3'!$B$6:$B$24,$A102,'S3'!$E$6:$E$24,"Víctor")+COUNTIFS('S3'!$B$6:$B$24,$A102,'S3'!$E$6:$E$24,"Ambos")+COUNTIFS('S4'!$B$6:$B$22,$A102,'S4'!$E$6:$E$22,"Víctor")+COUNTIFS('S4'!$B$6:$B$22,$A102,'S4'!$E$6:$E$22,"Ambos")+COUNTIFS('S5'!$B$6:$B$20,$A102,'S5'!$E$6:$E$20,"Víctor")+COUNTIFS('S5'!$B$6:$B$20,$A102,'S5'!$E$6:$E$20,"Ambos")+COUNTIFS('S6'!$B$6:$B$17,$A102,'S6'!$E$6:$E$17,"Víctor")+COUNTIFS('S6'!$B$6:$B$17,$A102,'S6'!$E$6:$E$17,"Ambos")+COUNTIFS('S7'!$B$6:$B$19,$A102,'S7'!$E$6:$E$19,"Víctor")+COUNTIFS('S7'!$B$6:$B$19,$A102,'S7'!$E$6:$E$19,"Ambos")+COUNTIFS('S8'!$B$6:$B$23,$A102,'S8'!$E$6:$E$23,"Víctor")+COUNTIFS('S8'!$B$6:$B$23,$A102,'S8'!$E$6:$E$23,"Ambos")+COUNTIFS('S9'!$B$6:$B$15,$A102,'S9'!$E$6:$E$15,"Víctor")+COUNTIFS('S9'!$B$6:$B$15,$A102,'S9'!$E$6:$E$15,"Ambos")+COUNTIFS('S10'!$B$6:$B$13,$A102,'S10'!$E$6:$E$13,"Víctor")+COUNTIFS('S10'!$B$6:$B$13,$A102,'S10'!$E$6:$E$13,"Ambos")+COUNTIFS('Holgura'!$B$6:$B$11,$A102,'Holgura'!$E$6:$E$11,"Víctor")+COUNTIFS('Holgura'!$B$6:$B$11,$A102,'Holgura'!$E$6:$E$11,"Ambos")+COUNTIFS('Entrega'!$B$6:$B$9,$A102,'Entrega'!$E$6:$E$9,"Víctor")+COUNTIFS('Entrega'!$B$6:$B$9,$A102,'Entrega'!$E$6:$E$9,"Ambos")+COUNTIFS('Defensa'!$B$6:$B$10,$A102,'Defensa'!$E$6:$E$10,"Víctor")+COUNTIFS('Defensa'!$B$6:$B$10,$A102,'Defensa'!$E$6:$E$10,"Ambos")</f>
         <v/>
       </c>
       <c r="G102" s="21">
-        <f>COUNTIFS('S1'!$B$6:$B$32,$A102,'S1'!$E$6:$E$32,"Diego")+COUNTIFS('S1'!$B$6:$B$32,$A102,'S1'!$E$6:$E$32,"Ambos")+COUNTIFS('S2'!$B$6:$B$23,$A102,'S2'!$E$6:$E$23,"Diego")+COUNTIFS('S2'!$B$6:$B$23,$A102,'S2'!$E$6:$E$23,"Ambos")+COUNTIFS('S3'!$B$6:$B$19,$A102,'S3'!$E$6:$E$19,"Diego")+COUNTIFS('S3'!$B$6:$B$19,$A102,'S3'!$E$6:$E$19,"Ambos")+COUNTIFS('S4'!$B$6:$B$20,$A102,'S4'!$E$6:$E$20,"Diego")+COUNTIFS('S4'!$B$6:$B$20,$A102,'S4'!$E$6:$E$20,"Ambos")+COUNTIFS('S5'!$B$6:$B$20,$A102,'S5'!$E$6:$E$20,"Diego")+COUNTIFS('S5'!$B$6:$B$20,$A102,'S5'!$E$6:$E$20,"Ambos")+COUNTIFS('S6'!$B$6:$B$17,$A102,'S6'!$E$6:$E$17,"Diego")+COUNTIFS('S6'!$B$6:$B$17,$A102,'S6'!$E$6:$E$17,"Ambos")+COUNTIFS('S7'!$B$6:$B$19,$A102,'S7'!$E$6:$E$19,"Diego")+COUNTIFS('S7'!$B$6:$B$19,$A102,'S7'!$E$6:$E$19,"Ambos")+COUNTIFS('S8'!$B$6:$B$23,$A102,'S8'!$E$6:$E$23,"Diego")+COUNTIFS('S8'!$B$6:$B$23,$A102,'S8'!$E$6:$E$23,"Ambos")+COUNTIFS('S9'!$B$6:$B$15,$A102,'S9'!$E$6:$E$15,"Diego")+COUNTIFS('S9'!$B$6:$B$15,$A102,'S9'!$E$6:$E$15,"Ambos")+COUNTIFS('S10'!$B$6:$B$13,$A102,'S10'!$E$6:$E$13,"Diego")+COUNTIFS('S10'!$B$6:$B$13,$A102,'S10'!$E$6:$E$13,"Ambos")+COUNTIFS('Holgura'!$B$6:$B$11,$A102,'Holgura'!$E$6:$E$11,"Diego")+COUNTIFS('Holgura'!$B$6:$B$11,$A102,'Holgura'!$E$6:$E$11,"Ambos")+COUNTIFS('Entrega'!$B$6:$B$9,$A102,'Entrega'!$E$6:$E$9,"Diego")+COUNTIFS('Entrega'!$B$6:$B$9,$A102,'Entrega'!$E$6:$E$9,"Ambos")+COUNTIFS('Defensa'!$B$6:$B$10,$A102,'Defensa'!$E$6:$E$10,"Diego")+COUNTIFS('Defensa'!$B$6:$B$10,$A102,'Defensa'!$E$6:$E$10,"Ambos")</f>
+        <f>COUNTIFS('S1'!$B$6:$B$32,$A102,'S1'!$E$6:$E$32,"Diego")+COUNTIFS('S1'!$B$6:$B$32,$A102,'S1'!$E$6:$E$32,"Ambos")+COUNTIFS('S2'!$B$6:$B$23,$A102,'S2'!$E$6:$E$23,"Diego")+COUNTIFS('S2'!$B$6:$B$23,$A102,'S2'!$E$6:$E$23,"Ambos")+COUNTIFS('S3'!$B$6:$B$24,$A102,'S3'!$E$6:$E$24,"Diego")+COUNTIFS('S3'!$B$6:$B$24,$A102,'S3'!$E$6:$E$24,"Ambos")+COUNTIFS('S4'!$B$6:$B$22,$A102,'S4'!$E$6:$E$22,"Diego")+COUNTIFS('S4'!$B$6:$B$22,$A102,'S4'!$E$6:$E$22,"Ambos")+COUNTIFS('S5'!$B$6:$B$20,$A102,'S5'!$E$6:$E$20,"Diego")+COUNTIFS('S5'!$B$6:$B$20,$A102,'S5'!$E$6:$E$20,"Ambos")+COUNTIFS('S6'!$B$6:$B$17,$A102,'S6'!$E$6:$E$17,"Diego")+COUNTIFS('S6'!$B$6:$B$17,$A102,'S6'!$E$6:$E$17,"Ambos")+COUNTIFS('S7'!$B$6:$B$19,$A102,'S7'!$E$6:$E$19,"Diego")+COUNTIFS('S7'!$B$6:$B$19,$A102,'S7'!$E$6:$E$19,"Ambos")+COUNTIFS('S8'!$B$6:$B$23,$A102,'S8'!$E$6:$E$23,"Diego")+COUNTIFS('S8'!$B$6:$B$23,$A102,'S8'!$E$6:$E$23,"Ambos")+COUNTIFS('S9'!$B$6:$B$15,$A102,'S9'!$E$6:$E$15,"Diego")+COUNTIFS('S9'!$B$6:$B$15,$A102,'S9'!$E$6:$E$15,"Ambos")+COUNTIFS('S10'!$B$6:$B$13,$A102,'S10'!$E$6:$E$13,"Diego")+COUNTIFS('S10'!$B$6:$B$13,$A102,'S10'!$E$6:$E$13,"Ambos")+COUNTIFS('Holgura'!$B$6:$B$11,$A102,'Holgura'!$E$6:$E$11,"Diego")+COUNTIFS('Holgura'!$B$6:$B$11,$A102,'Holgura'!$E$6:$E$11,"Ambos")+COUNTIFS('Entrega'!$B$6:$B$9,$A102,'Entrega'!$E$6:$E$9,"Diego")+COUNTIFS('Entrega'!$B$6:$B$9,$A102,'Entrega'!$E$6:$E$9,"Ambos")+COUNTIFS('Defensa'!$B$6:$B$10,$A102,'Defensa'!$E$6:$E$10,"Diego")+COUNTIFS('Defensa'!$B$6:$B$10,$A102,'Defensa'!$E$6:$E$10,"Ambos")</f>
         <v/>
       </c>
     </row>
@@ -11522,19 +11543,19 @@
         <v/>
       </c>
       <c r="D103" s="21">
-        <f>SUMIFS('S1'!$I$6:$I$32,'S1'!$B$6:$B$32,$A103,'S1'!$E$6:$E$32,"Víctor")+SUMIFS('S1'!$I$6:$I$32,'S1'!$B$6:$B$32,$A103,'S1'!$E$6:$E$32,"Ambos")+SUMIFS('S2'!$I$6:$I$23,'S2'!$B$6:$B$23,$A103,'S2'!$E$6:$E$23,"Víctor")+SUMIFS('S2'!$I$6:$I$23,'S2'!$B$6:$B$23,$A103,'S2'!$E$6:$E$23,"Ambos")+SUMIFS('S3'!$I$6:$I$19,'S3'!$B$6:$B$19,$A103,'S3'!$E$6:$E$19,"Víctor")+SUMIFS('S3'!$I$6:$I$19,'S3'!$B$6:$B$19,$A103,'S3'!$E$6:$E$19,"Ambos")+SUMIFS('S4'!$I$6:$I$20,'S4'!$B$6:$B$20,$A103,'S4'!$E$6:$E$20,"Víctor")+SUMIFS('S4'!$I$6:$I$20,'S4'!$B$6:$B$20,$A103,'S4'!$E$6:$E$20,"Ambos")+SUMIFS('S5'!$I$6:$I$20,'S5'!$B$6:$B$20,$A103,'S5'!$E$6:$E$20,"Víctor")+SUMIFS('S5'!$I$6:$I$20,'S5'!$B$6:$B$20,$A103,'S5'!$E$6:$E$20,"Ambos")+SUMIFS('S6'!$I$6:$I$17,'S6'!$B$6:$B$17,$A103,'S6'!$E$6:$E$17,"Víctor")+SUMIFS('S6'!$I$6:$I$17,'S6'!$B$6:$B$17,$A103,'S6'!$E$6:$E$17,"Ambos")+SUMIFS('S7'!$I$6:$I$19,'S7'!$B$6:$B$19,$A103,'S7'!$E$6:$E$19,"Víctor")+SUMIFS('S7'!$I$6:$I$19,'S7'!$B$6:$B$19,$A103,'S7'!$E$6:$E$19,"Ambos")+SUMIFS('S8'!$I$6:$I$23,'S8'!$B$6:$B$23,$A103,'S8'!$E$6:$E$23,"Víctor")+SUMIFS('S8'!$I$6:$I$23,'S8'!$B$6:$B$23,$A103,'S8'!$E$6:$E$23,"Ambos")+SUMIFS('S9'!$I$6:$I$15,'S9'!$B$6:$B$15,$A103,'S9'!$E$6:$E$15,"Víctor")+SUMIFS('S9'!$I$6:$I$15,'S9'!$B$6:$B$15,$A103,'S9'!$E$6:$E$15,"Ambos")+SUMIFS('S10'!$I$6:$I$13,'S10'!$B$6:$B$13,$A103,'S10'!$E$6:$E$13,"Víctor")+SUMIFS('S10'!$I$6:$I$13,'S10'!$B$6:$B$13,$A103,'S10'!$E$6:$E$13,"Ambos")+SUMIFS('Holgura'!$I$6:$I$11,'Holgura'!$B$6:$B$11,$A103,'Holgura'!$E$6:$E$11,"Víctor")+SUMIFS('Holgura'!$I$6:$I$11,'Holgura'!$B$6:$B$11,$A103,'Holgura'!$E$6:$E$11,"Ambos")+SUMIFS('Entrega'!$I$6:$I$9,'Entrega'!$B$6:$B$9,$A103,'Entrega'!$E$6:$E$9,"Víctor")+SUMIFS('Entrega'!$I$6:$I$9,'Entrega'!$B$6:$B$9,$A103,'Entrega'!$E$6:$E$9,"Ambos")+SUMIFS('Defensa'!$I$6:$I$10,'Defensa'!$B$6:$B$10,$A103,'Defensa'!$E$6:$E$10,"Víctor")+SUMIFS('Defensa'!$I$6:$I$10,'Defensa'!$B$6:$B$10,$A103,'Defensa'!$E$6:$E$10,"Ambos")</f>
+        <f>SUMIFS('S1'!$I$6:$I$32,'S1'!$B$6:$B$32,$A103,'S1'!$E$6:$E$32,"Víctor")+SUMIFS('S1'!$I$6:$I$32,'S1'!$B$6:$B$32,$A103,'S1'!$E$6:$E$32,"Ambos")+SUMIFS('S2'!$I$6:$I$23,'S2'!$B$6:$B$23,$A103,'S2'!$E$6:$E$23,"Víctor")+SUMIFS('S2'!$I$6:$I$23,'S2'!$B$6:$B$23,$A103,'S2'!$E$6:$E$23,"Ambos")+SUMIFS('S3'!$I$6:$I$24,'S3'!$B$6:$B$24,$A103,'S3'!$E$6:$E$24,"Víctor")+SUMIFS('S3'!$I$6:$I$24,'S3'!$B$6:$B$24,$A103,'S3'!$E$6:$E$24,"Ambos")+SUMIFS('S4'!$I$6:$I$22,'S4'!$B$6:$B$22,$A103,'S4'!$E$6:$E$22,"Víctor")+SUMIFS('S4'!$I$6:$I$22,'S4'!$B$6:$B$22,$A103,'S4'!$E$6:$E$22,"Ambos")+SUMIFS('S5'!$I$6:$I$20,'S5'!$B$6:$B$20,$A103,'S5'!$E$6:$E$20,"Víctor")+SUMIFS('S5'!$I$6:$I$20,'S5'!$B$6:$B$20,$A103,'S5'!$E$6:$E$20,"Ambos")+SUMIFS('S6'!$I$6:$I$17,'S6'!$B$6:$B$17,$A103,'S6'!$E$6:$E$17,"Víctor")+SUMIFS('S6'!$I$6:$I$17,'S6'!$B$6:$B$17,$A103,'S6'!$E$6:$E$17,"Ambos")+SUMIFS('S7'!$I$6:$I$19,'S7'!$B$6:$B$19,$A103,'S7'!$E$6:$E$19,"Víctor")+SUMIFS('S7'!$I$6:$I$19,'S7'!$B$6:$B$19,$A103,'S7'!$E$6:$E$19,"Ambos")+SUMIFS('S8'!$I$6:$I$23,'S8'!$B$6:$B$23,$A103,'S8'!$E$6:$E$23,"Víctor")+SUMIFS('S8'!$I$6:$I$23,'S8'!$B$6:$B$23,$A103,'S8'!$E$6:$E$23,"Ambos")+SUMIFS('S9'!$I$6:$I$15,'S9'!$B$6:$B$15,$A103,'S9'!$E$6:$E$15,"Víctor")+SUMIFS('S9'!$I$6:$I$15,'S9'!$B$6:$B$15,$A103,'S9'!$E$6:$E$15,"Ambos")+SUMIFS('S10'!$I$6:$I$13,'S10'!$B$6:$B$13,$A103,'S10'!$E$6:$E$13,"Víctor")+SUMIFS('S10'!$I$6:$I$13,'S10'!$B$6:$B$13,$A103,'S10'!$E$6:$E$13,"Ambos")+SUMIFS('Holgura'!$I$6:$I$11,'Holgura'!$B$6:$B$11,$A103,'Holgura'!$E$6:$E$11,"Víctor")+SUMIFS('Holgura'!$I$6:$I$11,'Holgura'!$B$6:$B$11,$A103,'Holgura'!$E$6:$E$11,"Ambos")+SUMIFS('Entrega'!$I$6:$I$9,'Entrega'!$B$6:$B$9,$A103,'Entrega'!$E$6:$E$9,"Víctor")+SUMIFS('Entrega'!$I$6:$I$9,'Entrega'!$B$6:$B$9,$A103,'Entrega'!$E$6:$E$9,"Ambos")+SUMIFS('Defensa'!$I$6:$I$10,'Defensa'!$B$6:$B$10,$A103,'Defensa'!$E$6:$E$10,"Víctor")+SUMIFS('Defensa'!$I$6:$I$10,'Defensa'!$B$6:$B$10,$A103,'Defensa'!$E$6:$E$10,"Ambos")</f>
         <v/>
       </c>
       <c r="E103" s="21">
-        <f>SUMIFS('S1'!$I$6:$I$32,'S1'!$B$6:$B$32,$A103,'S1'!$E$6:$E$32,"Diego")+SUMIFS('S1'!$I$6:$I$32,'S1'!$B$6:$B$32,$A103,'S1'!$E$6:$E$32,"Ambos")+SUMIFS('S2'!$I$6:$I$23,'S2'!$B$6:$B$23,$A103,'S2'!$E$6:$E$23,"Diego")+SUMIFS('S2'!$I$6:$I$23,'S2'!$B$6:$B$23,$A103,'S2'!$E$6:$E$23,"Ambos")+SUMIFS('S3'!$I$6:$I$19,'S3'!$B$6:$B$19,$A103,'S3'!$E$6:$E$19,"Diego")+SUMIFS('S3'!$I$6:$I$19,'S3'!$B$6:$B$19,$A103,'S3'!$E$6:$E$19,"Ambos")+SUMIFS('S4'!$I$6:$I$20,'S4'!$B$6:$B$20,$A103,'S4'!$E$6:$E$20,"Diego")+SUMIFS('S4'!$I$6:$I$20,'S4'!$B$6:$B$20,$A103,'S4'!$E$6:$E$20,"Ambos")+SUMIFS('S5'!$I$6:$I$20,'S5'!$B$6:$B$20,$A103,'S5'!$E$6:$E$20,"Diego")+SUMIFS('S5'!$I$6:$I$20,'S5'!$B$6:$B$20,$A103,'S5'!$E$6:$E$20,"Ambos")+SUMIFS('S6'!$I$6:$I$17,'S6'!$B$6:$B$17,$A103,'S6'!$E$6:$E$17,"Diego")+SUMIFS('S6'!$I$6:$I$17,'S6'!$B$6:$B$17,$A103,'S6'!$E$6:$E$17,"Ambos")+SUMIFS('S7'!$I$6:$I$19,'S7'!$B$6:$B$19,$A103,'S7'!$E$6:$E$19,"Diego")+SUMIFS('S7'!$I$6:$I$19,'S7'!$B$6:$B$19,$A103,'S7'!$E$6:$E$19,"Ambos")+SUMIFS('S8'!$I$6:$I$23,'S8'!$B$6:$B$23,$A103,'S8'!$E$6:$E$23,"Diego")+SUMIFS('S8'!$I$6:$I$23,'S8'!$B$6:$B$23,$A103,'S8'!$E$6:$E$23,"Ambos")+SUMIFS('S9'!$I$6:$I$15,'S9'!$B$6:$B$15,$A103,'S9'!$E$6:$E$15,"Diego")+SUMIFS('S9'!$I$6:$I$15,'S9'!$B$6:$B$15,$A103,'S9'!$E$6:$E$15,"Ambos")+SUMIFS('S10'!$I$6:$I$13,'S10'!$B$6:$B$13,$A103,'S10'!$E$6:$E$13,"Diego")+SUMIFS('S10'!$I$6:$I$13,'S10'!$B$6:$B$13,$A103,'S10'!$E$6:$E$13,"Ambos")+SUMIFS('Holgura'!$I$6:$I$11,'Holgura'!$B$6:$B$11,$A103,'Holgura'!$E$6:$E$11,"Diego")+SUMIFS('Holgura'!$I$6:$I$11,'Holgura'!$B$6:$B$11,$A103,'Holgura'!$E$6:$E$11,"Ambos")+SUMIFS('Entrega'!$I$6:$I$9,'Entrega'!$B$6:$B$9,$A103,'Entrega'!$E$6:$E$9,"Diego")+SUMIFS('Entrega'!$I$6:$I$9,'Entrega'!$B$6:$B$9,$A103,'Entrega'!$E$6:$E$9,"Ambos")+SUMIFS('Defensa'!$I$6:$I$10,'Defensa'!$B$6:$B$10,$A103,'Defensa'!$E$6:$E$10,"Diego")+SUMIFS('Defensa'!$I$6:$I$10,'Defensa'!$B$6:$B$10,$A103,'Defensa'!$E$6:$E$10,"Ambos")</f>
+        <f>SUMIFS('S1'!$I$6:$I$32,'S1'!$B$6:$B$32,$A103,'S1'!$E$6:$E$32,"Diego")+SUMIFS('S1'!$I$6:$I$32,'S1'!$B$6:$B$32,$A103,'S1'!$E$6:$E$32,"Ambos")+SUMIFS('S2'!$I$6:$I$23,'S2'!$B$6:$B$23,$A103,'S2'!$E$6:$E$23,"Diego")+SUMIFS('S2'!$I$6:$I$23,'S2'!$B$6:$B$23,$A103,'S2'!$E$6:$E$23,"Ambos")+SUMIFS('S3'!$I$6:$I$24,'S3'!$B$6:$B$24,$A103,'S3'!$E$6:$E$24,"Diego")+SUMIFS('S3'!$I$6:$I$24,'S3'!$B$6:$B$24,$A103,'S3'!$E$6:$E$24,"Ambos")+SUMIFS('S4'!$I$6:$I$22,'S4'!$B$6:$B$22,$A103,'S4'!$E$6:$E$22,"Diego")+SUMIFS('S4'!$I$6:$I$22,'S4'!$B$6:$B$22,$A103,'S4'!$E$6:$E$22,"Ambos")+SUMIFS('S5'!$I$6:$I$20,'S5'!$B$6:$B$20,$A103,'S5'!$E$6:$E$20,"Diego")+SUMIFS('S5'!$I$6:$I$20,'S5'!$B$6:$B$20,$A103,'S5'!$E$6:$E$20,"Ambos")+SUMIFS('S6'!$I$6:$I$17,'S6'!$B$6:$B$17,$A103,'S6'!$E$6:$E$17,"Diego")+SUMIFS('S6'!$I$6:$I$17,'S6'!$B$6:$B$17,$A103,'S6'!$E$6:$E$17,"Ambos")+SUMIFS('S7'!$I$6:$I$19,'S7'!$B$6:$B$19,$A103,'S7'!$E$6:$E$19,"Diego")+SUMIFS('S7'!$I$6:$I$19,'S7'!$B$6:$B$19,$A103,'S7'!$E$6:$E$19,"Ambos")+SUMIFS('S8'!$I$6:$I$23,'S8'!$B$6:$B$23,$A103,'S8'!$E$6:$E$23,"Diego")+SUMIFS('S8'!$I$6:$I$23,'S8'!$B$6:$B$23,$A103,'S8'!$E$6:$E$23,"Ambos")+SUMIFS('S9'!$I$6:$I$15,'S9'!$B$6:$B$15,$A103,'S9'!$E$6:$E$15,"Diego")+SUMIFS('S9'!$I$6:$I$15,'S9'!$B$6:$B$15,$A103,'S9'!$E$6:$E$15,"Ambos")+SUMIFS('S10'!$I$6:$I$13,'S10'!$B$6:$B$13,$A103,'S10'!$E$6:$E$13,"Diego")+SUMIFS('S10'!$I$6:$I$13,'S10'!$B$6:$B$13,$A103,'S10'!$E$6:$E$13,"Ambos")+SUMIFS('Holgura'!$I$6:$I$11,'Holgura'!$B$6:$B$11,$A103,'Holgura'!$E$6:$E$11,"Diego")+SUMIFS('Holgura'!$I$6:$I$11,'Holgura'!$B$6:$B$11,$A103,'Holgura'!$E$6:$E$11,"Ambos")+SUMIFS('Entrega'!$I$6:$I$9,'Entrega'!$B$6:$B$9,$A103,'Entrega'!$E$6:$E$9,"Diego")+SUMIFS('Entrega'!$I$6:$I$9,'Entrega'!$B$6:$B$9,$A103,'Entrega'!$E$6:$E$9,"Ambos")+SUMIFS('Defensa'!$I$6:$I$10,'Defensa'!$B$6:$B$10,$A103,'Defensa'!$E$6:$E$10,"Diego")+SUMIFS('Defensa'!$I$6:$I$10,'Defensa'!$B$6:$B$10,$A103,'Defensa'!$E$6:$E$10,"Ambos")</f>
         <v/>
       </c>
       <c r="F103" s="21">
-        <f>COUNTIFS('S1'!$B$6:$B$32,$A103,'S1'!$E$6:$E$32,"Víctor")+COUNTIFS('S1'!$B$6:$B$32,$A103,'S1'!$E$6:$E$32,"Ambos")+COUNTIFS('S2'!$B$6:$B$23,$A103,'S2'!$E$6:$E$23,"Víctor")+COUNTIFS('S2'!$B$6:$B$23,$A103,'S2'!$E$6:$E$23,"Ambos")+COUNTIFS('S3'!$B$6:$B$19,$A103,'S3'!$E$6:$E$19,"Víctor")+COUNTIFS('S3'!$B$6:$B$19,$A103,'S3'!$E$6:$E$19,"Ambos")+COUNTIFS('S4'!$B$6:$B$20,$A103,'S4'!$E$6:$E$20,"Víctor")+COUNTIFS('S4'!$B$6:$B$20,$A103,'S4'!$E$6:$E$20,"Ambos")+COUNTIFS('S5'!$B$6:$B$20,$A103,'S5'!$E$6:$E$20,"Víctor")+COUNTIFS('S5'!$B$6:$B$20,$A103,'S5'!$E$6:$E$20,"Ambos")+COUNTIFS('S6'!$B$6:$B$17,$A103,'S6'!$E$6:$E$17,"Víctor")+COUNTIFS('S6'!$B$6:$B$17,$A103,'S6'!$E$6:$E$17,"Ambos")+COUNTIFS('S7'!$B$6:$B$19,$A103,'S7'!$E$6:$E$19,"Víctor")+COUNTIFS('S7'!$B$6:$B$19,$A103,'S7'!$E$6:$E$19,"Ambos")+COUNTIFS('S8'!$B$6:$B$23,$A103,'S8'!$E$6:$E$23,"Víctor")+COUNTIFS('S8'!$B$6:$B$23,$A103,'S8'!$E$6:$E$23,"Ambos")+COUNTIFS('S9'!$B$6:$B$15,$A103,'S9'!$E$6:$E$15,"Víctor")+COUNTIFS('S9'!$B$6:$B$15,$A103,'S9'!$E$6:$E$15,"Ambos")+COUNTIFS('S10'!$B$6:$B$13,$A103,'S10'!$E$6:$E$13,"Víctor")+COUNTIFS('S10'!$B$6:$B$13,$A103,'S10'!$E$6:$E$13,"Ambos")+COUNTIFS('Holgura'!$B$6:$B$11,$A103,'Holgura'!$E$6:$E$11,"Víctor")+COUNTIFS('Holgura'!$B$6:$B$11,$A103,'Holgura'!$E$6:$E$11,"Ambos")+COUNTIFS('Entrega'!$B$6:$B$9,$A103,'Entrega'!$E$6:$E$9,"Víctor")+COUNTIFS('Entrega'!$B$6:$B$9,$A103,'Entrega'!$E$6:$E$9,"Ambos")+COUNTIFS('Defensa'!$B$6:$B$10,$A103,'Defensa'!$E$6:$E$10,"Víctor")+COUNTIFS('Defensa'!$B$6:$B$10,$A103,'Defensa'!$E$6:$E$10,"Ambos")</f>
+        <f>COUNTIFS('S1'!$B$6:$B$32,$A103,'S1'!$E$6:$E$32,"Víctor")+COUNTIFS('S1'!$B$6:$B$32,$A103,'S1'!$E$6:$E$32,"Ambos")+COUNTIFS('S2'!$B$6:$B$23,$A103,'S2'!$E$6:$E$23,"Víctor")+COUNTIFS('S2'!$B$6:$B$23,$A103,'S2'!$E$6:$E$23,"Ambos")+COUNTIFS('S3'!$B$6:$B$24,$A103,'S3'!$E$6:$E$24,"Víctor")+COUNTIFS('S3'!$B$6:$B$24,$A103,'S3'!$E$6:$E$24,"Ambos")+COUNTIFS('S4'!$B$6:$B$22,$A103,'S4'!$E$6:$E$22,"Víctor")+COUNTIFS('S4'!$B$6:$B$22,$A103,'S4'!$E$6:$E$22,"Ambos")+COUNTIFS('S5'!$B$6:$B$20,$A103,'S5'!$E$6:$E$20,"Víctor")+COUNTIFS('S5'!$B$6:$B$20,$A103,'S5'!$E$6:$E$20,"Ambos")+COUNTIFS('S6'!$B$6:$B$17,$A103,'S6'!$E$6:$E$17,"Víctor")+COUNTIFS('S6'!$B$6:$B$17,$A103,'S6'!$E$6:$E$17,"Ambos")+COUNTIFS('S7'!$B$6:$B$19,$A103,'S7'!$E$6:$E$19,"Víctor")+COUNTIFS('S7'!$B$6:$B$19,$A103,'S7'!$E$6:$E$19,"Ambos")+COUNTIFS('S8'!$B$6:$B$23,$A103,'S8'!$E$6:$E$23,"Víctor")+COUNTIFS('S8'!$B$6:$B$23,$A103,'S8'!$E$6:$E$23,"Ambos")+COUNTIFS('S9'!$B$6:$B$15,$A103,'S9'!$E$6:$E$15,"Víctor")+COUNTIFS('S9'!$B$6:$B$15,$A103,'S9'!$E$6:$E$15,"Ambos")+COUNTIFS('S10'!$B$6:$B$13,$A103,'S10'!$E$6:$E$13,"Víctor")+COUNTIFS('S10'!$B$6:$B$13,$A103,'S10'!$E$6:$E$13,"Ambos")+COUNTIFS('Holgura'!$B$6:$B$11,$A103,'Holgura'!$E$6:$E$11,"Víctor")+COUNTIFS('Holgura'!$B$6:$B$11,$A103,'Holgura'!$E$6:$E$11,"Ambos")+COUNTIFS('Entrega'!$B$6:$B$9,$A103,'Entrega'!$E$6:$E$9,"Víctor")+COUNTIFS('Entrega'!$B$6:$B$9,$A103,'Entrega'!$E$6:$E$9,"Ambos")+COUNTIFS('Defensa'!$B$6:$B$10,$A103,'Defensa'!$E$6:$E$10,"Víctor")+COUNTIFS('Defensa'!$B$6:$B$10,$A103,'Defensa'!$E$6:$E$10,"Ambos")</f>
         <v/>
       </c>
       <c r="G103" s="21">
-        <f>COUNTIFS('S1'!$B$6:$B$32,$A103,'S1'!$E$6:$E$32,"Diego")+COUNTIFS('S1'!$B$6:$B$32,$A103,'S1'!$E$6:$E$32,"Ambos")+COUNTIFS('S2'!$B$6:$B$23,$A103,'S2'!$E$6:$E$23,"Diego")+COUNTIFS('S2'!$B$6:$B$23,$A103,'S2'!$E$6:$E$23,"Ambos")+COUNTIFS('S3'!$B$6:$B$19,$A103,'S3'!$E$6:$E$19,"Diego")+COUNTIFS('S3'!$B$6:$B$19,$A103,'S3'!$E$6:$E$19,"Ambos")+COUNTIFS('S4'!$B$6:$B$20,$A103,'S4'!$E$6:$E$20,"Diego")+COUNTIFS('S4'!$B$6:$B$20,$A103,'S4'!$E$6:$E$20,"Ambos")+COUNTIFS('S5'!$B$6:$B$20,$A103,'S5'!$E$6:$E$20,"Diego")+COUNTIFS('S5'!$B$6:$B$20,$A103,'S5'!$E$6:$E$20,"Ambos")+COUNTIFS('S6'!$B$6:$B$17,$A103,'S6'!$E$6:$E$17,"Diego")+COUNTIFS('S6'!$B$6:$B$17,$A103,'S6'!$E$6:$E$17,"Ambos")+COUNTIFS('S7'!$B$6:$B$19,$A103,'S7'!$E$6:$E$19,"Diego")+COUNTIFS('S7'!$B$6:$B$19,$A103,'S7'!$E$6:$E$19,"Ambos")+COUNTIFS('S8'!$B$6:$B$23,$A103,'S8'!$E$6:$E$23,"Diego")+COUNTIFS('S8'!$B$6:$B$23,$A103,'S8'!$E$6:$E$23,"Ambos")+COUNTIFS('S9'!$B$6:$B$15,$A103,'S9'!$E$6:$E$15,"Diego")+COUNTIFS('S9'!$B$6:$B$15,$A103,'S9'!$E$6:$E$15,"Ambos")+COUNTIFS('S10'!$B$6:$B$13,$A103,'S10'!$E$6:$E$13,"Diego")+COUNTIFS('S10'!$B$6:$B$13,$A103,'S10'!$E$6:$E$13,"Ambos")+COUNTIFS('Holgura'!$B$6:$B$11,$A103,'Holgura'!$E$6:$E$11,"Diego")+COUNTIFS('Holgura'!$B$6:$B$11,$A103,'Holgura'!$E$6:$E$11,"Ambos")+COUNTIFS('Entrega'!$B$6:$B$9,$A103,'Entrega'!$E$6:$E$9,"Diego")+COUNTIFS('Entrega'!$B$6:$B$9,$A103,'Entrega'!$E$6:$E$9,"Ambos")+COUNTIFS('Defensa'!$B$6:$B$10,$A103,'Defensa'!$E$6:$E$10,"Diego")+COUNTIFS('Defensa'!$B$6:$B$10,$A103,'Defensa'!$E$6:$E$10,"Ambos")</f>
+        <f>COUNTIFS('S1'!$B$6:$B$32,$A103,'S1'!$E$6:$E$32,"Diego")+COUNTIFS('S1'!$B$6:$B$32,$A103,'S1'!$E$6:$E$32,"Ambos")+COUNTIFS('S2'!$B$6:$B$23,$A103,'S2'!$E$6:$E$23,"Diego")+COUNTIFS('S2'!$B$6:$B$23,$A103,'S2'!$E$6:$E$23,"Ambos")+COUNTIFS('S3'!$B$6:$B$24,$A103,'S3'!$E$6:$E$24,"Diego")+COUNTIFS('S3'!$B$6:$B$24,$A103,'S3'!$E$6:$E$24,"Ambos")+COUNTIFS('S4'!$B$6:$B$22,$A103,'S4'!$E$6:$E$22,"Diego")+COUNTIFS('S4'!$B$6:$B$22,$A103,'S4'!$E$6:$E$22,"Ambos")+COUNTIFS('S5'!$B$6:$B$20,$A103,'S5'!$E$6:$E$20,"Diego")+COUNTIFS('S5'!$B$6:$B$20,$A103,'S5'!$E$6:$E$20,"Ambos")+COUNTIFS('S6'!$B$6:$B$17,$A103,'S6'!$E$6:$E$17,"Diego")+COUNTIFS('S6'!$B$6:$B$17,$A103,'S6'!$E$6:$E$17,"Ambos")+COUNTIFS('S7'!$B$6:$B$19,$A103,'S7'!$E$6:$E$19,"Diego")+COUNTIFS('S7'!$B$6:$B$19,$A103,'S7'!$E$6:$E$19,"Ambos")+COUNTIFS('S8'!$B$6:$B$23,$A103,'S8'!$E$6:$E$23,"Diego")+COUNTIFS('S8'!$B$6:$B$23,$A103,'S8'!$E$6:$E$23,"Ambos")+COUNTIFS('S9'!$B$6:$B$15,$A103,'S9'!$E$6:$E$15,"Diego")+COUNTIFS('S9'!$B$6:$B$15,$A103,'S9'!$E$6:$E$15,"Ambos")+COUNTIFS('S10'!$B$6:$B$13,$A103,'S10'!$E$6:$E$13,"Diego")+COUNTIFS('S10'!$B$6:$B$13,$A103,'S10'!$E$6:$E$13,"Ambos")+COUNTIFS('Holgura'!$B$6:$B$11,$A103,'Holgura'!$E$6:$E$11,"Diego")+COUNTIFS('Holgura'!$B$6:$B$11,$A103,'Holgura'!$E$6:$E$11,"Ambos")+COUNTIFS('Entrega'!$B$6:$B$9,$A103,'Entrega'!$E$6:$E$9,"Diego")+COUNTIFS('Entrega'!$B$6:$B$9,$A103,'Entrega'!$E$6:$E$9,"Ambos")+COUNTIFS('Defensa'!$B$6:$B$10,$A103,'Defensa'!$E$6:$E$10,"Diego")+COUNTIFS('Defensa'!$B$6:$B$10,$A103,'Defensa'!$E$6:$E$10,"Ambos")</f>
         <v/>
       </c>
     </row>
@@ -11551,19 +11572,19 @@
         <v/>
       </c>
       <c r="D104" s="21">
-        <f>SUMIFS('S1'!$I$6:$I$32,'S1'!$B$6:$B$32,$A104,'S1'!$E$6:$E$32,"Víctor")+SUMIFS('S1'!$I$6:$I$32,'S1'!$B$6:$B$32,$A104,'S1'!$E$6:$E$32,"Ambos")+SUMIFS('S2'!$I$6:$I$23,'S2'!$B$6:$B$23,$A104,'S2'!$E$6:$E$23,"Víctor")+SUMIFS('S2'!$I$6:$I$23,'S2'!$B$6:$B$23,$A104,'S2'!$E$6:$E$23,"Ambos")+SUMIFS('S3'!$I$6:$I$19,'S3'!$B$6:$B$19,$A104,'S3'!$E$6:$E$19,"Víctor")+SUMIFS('S3'!$I$6:$I$19,'S3'!$B$6:$B$19,$A104,'S3'!$E$6:$E$19,"Ambos")+SUMIFS('S4'!$I$6:$I$20,'S4'!$B$6:$B$20,$A104,'S4'!$E$6:$E$20,"Víctor")+SUMIFS('S4'!$I$6:$I$20,'S4'!$B$6:$B$20,$A104,'S4'!$E$6:$E$20,"Ambos")+SUMIFS('S5'!$I$6:$I$20,'S5'!$B$6:$B$20,$A104,'S5'!$E$6:$E$20,"Víctor")+SUMIFS('S5'!$I$6:$I$20,'S5'!$B$6:$B$20,$A104,'S5'!$E$6:$E$20,"Ambos")+SUMIFS('S6'!$I$6:$I$17,'S6'!$B$6:$B$17,$A104,'S6'!$E$6:$E$17,"Víctor")+SUMIFS('S6'!$I$6:$I$17,'S6'!$B$6:$B$17,$A104,'S6'!$E$6:$E$17,"Ambos")+SUMIFS('S7'!$I$6:$I$19,'S7'!$B$6:$B$19,$A104,'S7'!$E$6:$E$19,"Víctor")+SUMIFS('S7'!$I$6:$I$19,'S7'!$B$6:$B$19,$A104,'S7'!$E$6:$E$19,"Ambos")+SUMIFS('S8'!$I$6:$I$23,'S8'!$B$6:$B$23,$A104,'S8'!$E$6:$E$23,"Víctor")+SUMIFS('S8'!$I$6:$I$23,'S8'!$B$6:$B$23,$A104,'S8'!$E$6:$E$23,"Ambos")+SUMIFS('S9'!$I$6:$I$15,'S9'!$B$6:$B$15,$A104,'S9'!$E$6:$E$15,"Víctor")+SUMIFS('S9'!$I$6:$I$15,'S9'!$B$6:$B$15,$A104,'S9'!$E$6:$E$15,"Ambos")+SUMIFS('S10'!$I$6:$I$13,'S10'!$B$6:$B$13,$A104,'S10'!$E$6:$E$13,"Víctor")+SUMIFS('S10'!$I$6:$I$13,'S10'!$B$6:$B$13,$A104,'S10'!$E$6:$E$13,"Ambos")+SUMIFS('Holgura'!$I$6:$I$11,'Holgura'!$B$6:$B$11,$A104,'Holgura'!$E$6:$E$11,"Víctor")+SUMIFS('Holgura'!$I$6:$I$11,'Holgura'!$B$6:$B$11,$A104,'Holgura'!$E$6:$E$11,"Ambos")+SUMIFS('Entrega'!$I$6:$I$9,'Entrega'!$B$6:$B$9,$A104,'Entrega'!$E$6:$E$9,"Víctor")+SUMIFS('Entrega'!$I$6:$I$9,'Entrega'!$B$6:$B$9,$A104,'Entrega'!$E$6:$E$9,"Ambos")+SUMIFS('Defensa'!$I$6:$I$10,'Defensa'!$B$6:$B$10,$A104,'Defensa'!$E$6:$E$10,"Víctor")+SUMIFS('Defensa'!$I$6:$I$10,'Defensa'!$B$6:$B$10,$A104,'Defensa'!$E$6:$E$10,"Ambos")</f>
+        <f>SUMIFS('S1'!$I$6:$I$32,'S1'!$B$6:$B$32,$A104,'S1'!$E$6:$E$32,"Víctor")+SUMIFS('S1'!$I$6:$I$32,'S1'!$B$6:$B$32,$A104,'S1'!$E$6:$E$32,"Ambos")+SUMIFS('S2'!$I$6:$I$23,'S2'!$B$6:$B$23,$A104,'S2'!$E$6:$E$23,"Víctor")+SUMIFS('S2'!$I$6:$I$23,'S2'!$B$6:$B$23,$A104,'S2'!$E$6:$E$23,"Ambos")+SUMIFS('S3'!$I$6:$I$24,'S3'!$B$6:$B$24,$A104,'S3'!$E$6:$E$24,"Víctor")+SUMIFS('S3'!$I$6:$I$24,'S3'!$B$6:$B$24,$A104,'S3'!$E$6:$E$24,"Ambos")+SUMIFS('S4'!$I$6:$I$22,'S4'!$B$6:$B$22,$A104,'S4'!$E$6:$E$22,"Víctor")+SUMIFS('S4'!$I$6:$I$22,'S4'!$B$6:$B$22,$A104,'S4'!$E$6:$E$22,"Ambos")+SUMIFS('S5'!$I$6:$I$20,'S5'!$B$6:$B$20,$A104,'S5'!$E$6:$E$20,"Víctor")+SUMIFS('S5'!$I$6:$I$20,'S5'!$B$6:$B$20,$A104,'S5'!$E$6:$E$20,"Ambos")+SUMIFS('S6'!$I$6:$I$17,'S6'!$B$6:$B$17,$A104,'S6'!$E$6:$E$17,"Víctor")+SUMIFS('S6'!$I$6:$I$17,'S6'!$B$6:$B$17,$A104,'S6'!$E$6:$E$17,"Ambos")+SUMIFS('S7'!$I$6:$I$19,'S7'!$B$6:$B$19,$A104,'S7'!$E$6:$E$19,"Víctor")+SUMIFS('S7'!$I$6:$I$19,'S7'!$B$6:$B$19,$A104,'S7'!$E$6:$E$19,"Ambos")+SUMIFS('S8'!$I$6:$I$23,'S8'!$B$6:$B$23,$A104,'S8'!$E$6:$E$23,"Víctor")+SUMIFS('S8'!$I$6:$I$23,'S8'!$B$6:$B$23,$A104,'S8'!$E$6:$E$23,"Ambos")+SUMIFS('S9'!$I$6:$I$15,'S9'!$B$6:$B$15,$A104,'S9'!$E$6:$E$15,"Víctor")+SUMIFS('S9'!$I$6:$I$15,'S9'!$B$6:$B$15,$A104,'S9'!$E$6:$E$15,"Ambos")+SUMIFS('S10'!$I$6:$I$13,'S10'!$B$6:$B$13,$A104,'S10'!$E$6:$E$13,"Víctor")+SUMIFS('S10'!$I$6:$I$13,'S10'!$B$6:$B$13,$A104,'S10'!$E$6:$E$13,"Ambos")+SUMIFS('Holgura'!$I$6:$I$11,'Holgura'!$B$6:$B$11,$A104,'Holgura'!$E$6:$E$11,"Víctor")+SUMIFS('Holgura'!$I$6:$I$11,'Holgura'!$B$6:$B$11,$A104,'Holgura'!$E$6:$E$11,"Ambos")+SUMIFS('Entrega'!$I$6:$I$9,'Entrega'!$B$6:$B$9,$A104,'Entrega'!$E$6:$E$9,"Víctor")+SUMIFS('Entrega'!$I$6:$I$9,'Entrega'!$B$6:$B$9,$A104,'Entrega'!$E$6:$E$9,"Ambos")+SUMIFS('Defensa'!$I$6:$I$10,'Defensa'!$B$6:$B$10,$A104,'Defensa'!$E$6:$E$10,"Víctor")+SUMIFS('Defensa'!$I$6:$I$10,'Defensa'!$B$6:$B$10,$A104,'Defensa'!$E$6:$E$10,"Ambos")</f>
         <v/>
       </c>
       <c r="E104" s="21">
-        <f>SUMIFS('S1'!$I$6:$I$32,'S1'!$B$6:$B$32,$A104,'S1'!$E$6:$E$32,"Diego")+SUMIFS('S1'!$I$6:$I$32,'S1'!$B$6:$B$32,$A104,'S1'!$E$6:$E$32,"Ambos")+SUMIFS('S2'!$I$6:$I$23,'S2'!$B$6:$B$23,$A104,'S2'!$E$6:$E$23,"Diego")+SUMIFS('S2'!$I$6:$I$23,'S2'!$B$6:$B$23,$A104,'S2'!$E$6:$E$23,"Ambos")+SUMIFS('S3'!$I$6:$I$19,'S3'!$B$6:$B$19,$A104,'S3'!$E$6:$E$19,"Diego")+SUMIFS('S3'!$I$6:$I$19,'S3'!$B$6:$B$19,$A104,'S3'!$E$6:$E$19,"Ambos")+SUMIFS('S4'!$I$6:$I$20,'S4'!$B$6:$B$20,$A104,'S4'!$E$6:$E$20,"Diego")+SUMIFS('S4'!$I$6:$I$20,'S4'!$B$6:$B$20,$A104,'S4'!$E$6:$E$20,"Ambos")+SUMIFS('S5'!$I$6:$I$20,'S5'!$B$6:$B$20,$A104,'S5'!$E$6:$E$20,"Diego")+SUMIFS('S5'!$I$6:$I$20,'S5'!$B$6:$B$20,$A104,'S5'!$E$6:$E$20,"Ambos")+SUMIFS('S6'!$I$6:$I$17,'S6'!$B$6:$B$17,$A104,'S6'!$E$6:$E$17,"Diego")+SUMIFS('S6'!$I$6:$I$17,'S6'!$B$6:$B$17,$A104,'S6'!$E$6:$E$17,"Ambos")+SUMIFS('S7'!$I$6:$I$19,'S7'!$B$6:$B$19,$A104,'S7'!$E$6:$E$19,"Diego")+SUMIFS('S7'!$I$6:$I$19,'S7'!$B$6:$B$19,$A104,'S7'!$E$6:$E$19,"Ambos")+SUMIFS('S8'!$I$6:$I$23,'S8'!$B$6:$B$23,$A104,'S8'!$E$6:$E$23,"Diego")+SUMIFS('S8'!$I$6:$I$23,'S8'!$B$6:$B$23,$A104,'S8'!$E$6:$E$23,"Ambos")+SUMIFS('S9'!$I$6:$I$15,'S9'!$B$6:$B$15,$A104,'S9'!$E$6:$E$15,"Diego")+SUMIFS('S9'!$I$6:$I$15,'S9'!$B$6:$B$15,$A104,'S9'!$E$6:$E$15,"Ambos")+SUMIFS('S10'!$I$6:$I$13,'S10'!$B$6:$B$13,$A104,'S10'!$E$6:$E$13,"Diego")+SUMIFS('S10'!$I$6:$I$13,'S10'!$B$6:$B$13,$A104,'S10'!$E$6:$E$13,"Ambos")+SUMIFS('Holgura'!$I$6:$I$11,'Holgura'!$B$6:$B$11,$A104,'Holgura'!$E$6:$E$11,"Diego")+SUMIFS('Holgura'!$I$6:$I$11,'Holgura'!$B$6:$B$11,$A104,'Holgura'!$E$6:$E$11,"Ambos")+SUMIFS('Entrega'!$I$6:$I$9,'Entrega'!$B$6:$B$9,$A104,'Entrega'!$E$6:$E$9,"Diego")+SUMIFS('Entrega'!$I$6:$I$9,'Entrega'!$B$6:$B$9,$A104,'Entrega'!$E$6:$E$9,"Ambos")+SUMIFS('Defensa'!$I$6:$I$10,'Defensa'!$B$6:$B$10,$A104,'Defensa'!$E$6:$E$10,"Diego")+SUMIFS('Defensa'!$I$6:$I$10,'Defensa'!$B$6:$B$10,$A104,'Defensa'!$E$6:$E$10,"Ambos")</f>
+        <f>SUMIFS('S1'!$I$6:$I$32,'S1'!$B$6:$B$32,$A104,'S1'!$E$6:$E$32,"Diego")+SUMIFS('S1'!$I$6:$I$32,'S1'!$B$6:$B$32,$A104,'S1'!$E$6:$E$32,"Ambos")+SUMIFS('S2'!$I$6:$I$23,'S2'!$B$6:$B$23,$A104,'S2'!$E$6:$E$23,"Diego")+SUMIFS('S2'!$I$6:$I$23,'S2'!$B$6:$B$23,$A104,'S2'!$E$6:$E$23,"Ambos")+SUMIFS('S3'!$I$6:$I$24,'S3'!$B$6:$B$24,$A104,'S3'!$E$6:$E$24,"Diego")+SUMIFS('S3'!$I$6:$I$24,'S3'!$B$6:$B$24,$A104,'S3'!$E$6:$E$24,"Ambos")+SUMIFS('S4'!$I$6:$I$22,'S4'!$B$6:$B$22,$A104,'S4'!$E$6:$E$22,"Diego")+SUMIFS('S4'!$I$6:$I$22,'S4'!$B$6:$B$22,$A104,'S4'!$E$6:$E$22,"Ambos")+SUMIFS('S5'!$I$6:$I$20,'S5'!$B$6:$B$20,$A104,'S5'!$E$6:$E$20,"Diego")+SUMIFS('S5'!$I$6:$I$20,'S5'!$B$6:$B$20,$A104,'S5'!$E$6:$E$20,"Ambos")+SUMIFS('S6'!$I$6:$I$17,'S6'!$B$6:$B$17,$A104,'S6'!$E$6:$E$17,"Diego")+SUMIFS('S6'!$I$6:$I$17,'S6'!$B$6:$B$17,$A104,'S6'!$E$6:$E$17,"Ambos")+SUMIFS('S7'!$I$6:$I$19,'S7'!$B$6:$B$19,$A104,'S7'!$E$6:$E$19,"Diego")+SUMIFS('S7'!$I$6:$I$19,'S7'!$B$6:$B$19,$A104,'S7'!$E$6:$E$19,"Ambos")+SUMIFS('S8'!$I$6:$I$23,'S8'!$B$6:$B$23,$A104,'S8'!$E$6:$E$23,"Diego")+SUMIFS('S8'!$I$6:$I$23,'S8'!$B$6:$B$23,$A104,'S8'!$E$6:$E$23,"Ambos")+SUMIFS('S9'!$I$6:$I$15,'S9'!$B$6:$B$15,$A104,'S9'!$E$6:$E$15,"Diego")+SUMIFS('S9'!$I$6:$I$15,'S9'!$B$6:$B$15,$A104,'S9'!$E$6:$E$15,"Ambos")+SUMIFS('S10'!$I$6:$I$13,'S10'!$B$6:$B$13,$A104,'S10'!$E$6:$E$13,"Diego")+SUMIFS('S10'!$I$6:$I$13,'S10'!$B$6:$B$13,$A104,'S10'!$E$6:$E$13,"Ambos")+SUMIFS('Holgura'!$I$6:$I$11,'Holgura'!$B$6:$B$11,$A104,'Holgura'!$E$6:$E$11,"Diego")+SUMIFS('Holgura'!$I$6:$I$11,'Holgura'!$B$6:$B$11,$A104,'Holgura'!$E$6:$E$11,"Ambos")+SUMIFS('Entrega'!$I$6:$I$9,'Entrega'!$B$6:$B$9,$A104,'Entrega'!$E$6:$E$9,"Diego")+SUMIFS('Entrega'!$I$6:$I$9,'Entrega'!$B$6:$B$9,$A104,'Entrega'!$E$6:$E$9,"Ambos")+SUMIFS('Defensa'!$I$6:$I$10,'Defensa'!$B$6:$B$10,$A104,'Defensa'!$E$6:$E$10,"Diego")+SUMIFS('Defensa'!$I$6:$I$10,'Defensa'!$B$6:$B$10,$A104,'Defensa'!$E$6:$E$10,"Ambos")</f>
         <v/>
       </c>
       <c r="F104" s="21">
-        <f>COUNTIFS('S1'!$B$6:$B$32,$A104,'S1'!$E$6:$E$32,"Víctor")+COUNTIFS('S1'!$B$6:$B$32,$A104,'S1'!$E$6:$E$32,"Ambos")+COUNTIFS('S2'!$B$6:$B$23,$A104,'S2'!$E$6:$E$23,"Víctor")+COUNTIFS('S2'!$B$6:$B$23,$A104,'S2'!$E$6:$E$23,"Ambos")+COUNTIFS('S3'!$B$6:$B$19,$A104,'S3'!$E$6:$E$19,"Víctor")+COUNTIFS('S3'!$B$6:$B$19,$A104,'S3'!$E$6:$E$19,"Ambos")+COUNTIFS('S4'!$B$6:$B$20,$A104,'S4'!$E$6:$E$20,"Víctor")+COUNTIFS('S4'!$B$6:$B$20,$A104,'S4'!$E$6:$E$20,"Ambos")+COUNTIFS('S5'!$B$6:$B$20,$A104,'S5'!$E$6:$E$20,"Víctor")+COUNTIFS('S5'!$B$6:$B$20,$A104,'S5'!$E$6:$E$20,"Ambos")+COUNTIFS('S6'!$B$6:$B$17,$A104,'S6'!$E$6:$E$17,"Víctor")+COUNTIFS('S6'!$B$6:$B$17,$A104,'S6'!$E$6:$E$17,"Ambos")+COUNTIFS('S7'!$B$6:$B$19,$A104,'S7'!$E$6:$E$19,"Víctor")+COUNTIFS('S7'!$B$6:$B$19,$A104,'S7'!$E$6:$E$19,"Ambos")+COUNTIFS('S8'!$B$6:$B$23,$A104,'S8'!$E$6:$E$23,"Víctor")+COUNTIFS('S8'!$B$6:$B$23,$A104,'S8'!$E$6:$E$23,"Ambos")+COUNTIFS('S9'!$B$6:$B$15,$A104,'S9'!$E$6:$E$15,"Víctor")+COUNTIFS('S9'!$B$6:$B$15,$A104,'S9'!$E$6:$E$15,"Ambos")+COUNTIFS('S10'!$B$6:$B$13,$A104,'S10'!$E$6:$E$13,"Víctor")+COUNTIFS('S10'!$B$6:$B$13,$A104,'S10'!$E$6:$E$13,"Ambos")+COUNTIFS('Holgura'!$B$6:$B$11,$A104,'Holgura'!$E$6:$E$11,"Víctor")+COUNTIFS('Holgura'!$B$6:$B$11,$A104,'Holgura'!$E$6:$E$11,"Ambos")+COUNTIFS('Entrega'!$B$6:$B$9,$A104,'Entrega'!$E$6:$E$9,"Víctor")+COUNTIFS('Entrega'!$B$6:$B$9,$A104,'Entrega'!$E$6:$E$9,"Ambos")+COUNTIFS('Defensa'!$B$6:$B$10,$A104,'Defensa'!$E$6:$E$10,"Víctor")+COUNTIFS('Defensa'!$B$6:$B$10,$A104,'Defensa'!$E$6:$E$10,"Ambos")</f>
+        <f>COUNTIFS('S1'!$B$6:$B$32,$A104,'S1'!$E$6:$E$32,"Víctor")+COUNTIFS('S1'!$B$6:$B$32,$A104,'S1'!$E$6:$E$32,"Ambos")+COUNTIFS('S2'!$B$6:$B$23,$A104,'S2'!$E$6:$E$23,"Víctor")+COUNTIFS('S2'!$B$6:$B$23,$A104,'S2'!$E$6:$E$23,"Ambos")+COUNTIFS('S3'!$B$6:$B$24,$A104,'S3'!$E$6:$E$24,"Víctor")+COUNTIFS('S3'!$B$6:$B$24,$A104,'S3'!$E$6:$E$24,"Ambos")+COUNTIFS('S4'!$B$6:$B$22,$A104,'S4'!$E$6:$E$22,"Víctor")+COUNTIFS('S4'!$B$6:$B$22,$A104,'S4'!$E$6:$E$22,"Ambos")+COUNTIFS('S5'!$B$6:$B$20,$A104,'S5'!$E$6:$E$20,"Víctor")+COUNTIFS('S5'!$B$6:$B$20,$A104,'S5'!$E$6:$E$20,"Ambos")+COUNTIFS('S6'!$B$6:$B$17,$A104,'S6'!$E$6:$E$17,"Víctor")+COUNTIFS('S6'!$B$6:$B$17,$A104,'S6'!$E$6:$E$17,"Ambos")+COUNTIFS('S7'!$B$6:$B$19,$A104,'S7'!$E$6:$E$19,"Víctor")+COUNTIFS('S7'!$B$6:$B$19,$A104,'S7'!$E$6:$E$19,"Ambos")+COUNTIFS('S8'!$B$6:$B$23,$A104,'S8'!$E$6:$E$23,"Víctor")+COUNTIFS('S8'!$B$6:$B$23,$A104,'S8'!$E$6:$E$23,"Ambos")+COUNTIFS('S9'!$B$6:$B$15,$A104,'S9'!$E$6:$E$15,"Víctor")+COUNTIFS('S9'!$B$6:$B$15,$A104,'S9'!$E$6:$E$15,"Ambos")+COUNTIFS('S10'!$B$6:$B$13,$A104,'S10'!$E$6:$E$13,"Víctor")+COUNTIFS('S10'!$B$6:$B$13,$A104,'S10'!$E$6:$E$13,"Ambos")+COUNTIFS('Holgura'!$B$6:$B$11,$A104,'Holgura'!$E$6:$E$11,"Víctor")+COUNTIFS('Holgura'!$B$6:$B$11,$A104,'Holgura'!$E$6:$E$11,"Ambos")+COUNTIFS('Entrega'!$B$6:$B$9,$A104,'Entrega'!$E$6:$E$9,"Víctor")+COUNTIFS('Entrega'!$B$6:$B$9,$A104,'Entrega'!$E$6:$E$9,"Ambos")+COUNTIFS('Defensa'!$B$6:$B$10,$A104,'Defensa'!$E$6:$E$10,"Víctor")+COUNTIFS('Defensa'!$B$6:$B$10,$A104,'Defensa'!$E$6:$E$10,"Ambos")</f>
         <v/>
       </c>
       <c r="G104" s="21">
-        <f>COUNTIFS('S1'!$B$6:$B$32,$A104,'S1'!$E$6:$E$32,"Diego")+COUNTIFS('S1'!$B$6:$B$32,$A104,'S1'!$E$6:$E$32,"Ambos")+COUNTIFS('S2'!$B$6:$B$23,$A104,'S2'!$E$6:$E$23,"Diego")+COUNTIFS('S2'!$B$6:$B$23,$A104,'S2'!$E$6:$E$23,"Ambos")+COUNTIFS('S3'!$B$6:$B$19,$A104,'S3'!$E$6:$E$19,"Diego")+COUNTIFS('S3'!$B$6:$B$19,$A104,'S3'!$E$6:$E$19,"Ambos")+COUNTIFS('S4'!$B$6:$B$20,$A104,'S4'!$E$6:$E$20,"Diego")+COUNTIFS('S4'!$B$6:$B$20,$A104,'S4'!$E$6:$E$20,"Ambos")+COUNTIFS('S5'!$B$6:$B$20,$A104,'S5'!$E$6:$E$20,"Diego")+COUNTIFS('S5'!$B$6:$B$20,$A104,'S5'!$E$6:$E$20,"Ambos")+COUNTIFS('S6'!$B$6:$B$17,$A104,'S6'!$E$6:$E$17,"Diego")+COUNTIFS('S6'!$B$6:$B$17,$A104,'S6'!$E$6:$E$17,"Ambos")+COUNTIFS('S7'!$B$6:$B$19,$A104,'S7'!$E$6:$E$19,"Diego")+COUNTIFS('S7'!$B$6:$B$19,$A104,'S7'!$E$6:$E$19,"Ambos")+COUNTIFS('S8'!$B$6:$B$23,$A104,'S8'!$E$6:$E$23,"Diego")+COUNTIFS('S8'!$B$6:$B$23,$A104,'S8'!$E$6:$E$23,"Ambos")+COUNTIFS('S9'!$B$6:$B$15,$A104,'S9'!$E$6:$E$15,"Diego")+COUNTIFS('S9'!$B$6:$B$15,$A104,'S9'!$E$6:$E$15,"Ambos")+COUNTIFS('S10'!$B$6:$B$13,$A104,'S10'!$E$6:$E$13,"Diego")+COUNTIFS('S10'!$B$6:$B$13,$A104,'S10'!$E$6:$E$13,"Ambos")+COUNTIFS('Holgura'!$B$6:$B$11,$A104,'Holgura'!$E$6:$E$11,"Diego")+COUNTIFS('Holgura'!$B$6:$B$11,$A104,'Holgura'!$E$6:$E$11,"Ambos")+COUNTIFS('Entrega'!$B$6:$B$9,$A104,'Entrega'!$E$6:$E$9,"Diego")+COUNTIFS('Entrega'!$B$6:$B$9,$A104,'Entrega'!$E$6:$E$9,"Ambos")+COUNTIFS('Defensa'!$B$6:$B$10,$A104,'Defensa'!$E$6:$E$10,"Diego")+COUNTIFS('Defensa'!$B$6:$B$10,$A104,'Defensa'!$E$6:$E$10,"Ambos")</f>
+        <f>COUNTIFS('S1'!$B$6:$B$32,$A104,'S1'!$E$6:$E$32,"Diego")+COUNTIFS('S1'!$B$6:$B$32,$A104,'S1'!$E$6:$E$32,"Ambos")+COUNTIFS('S2'!$B$6:$B$23,$A104,'S2'!$E$6:$E$23,"Diego")+COUNTIFS('S2'!$B$6:$B$23,$A104,'S2'!$E$6:$E$23,"Ambos")+COUNTIFS('S3'!$B$6:$B$24,$A104,'S3'!$E$6:$E$24,"Diego")+COUNTIFS('S3'!$B$6:$B$24,$A104,'S3'!$E$6:$E$24,"Ambos")+COUNTIFS('S4'!$B$6:$B$22,$A104,'S4'!$E$6:$E$22,"Diego")+COUNTIFS('S4'!$B$6:$B$22,$A104,'S4'!$E$6:$E$22,"Ambos")+COUNTIFS('S5'!$B$6:$B$20,$A104,'S5'!$E$6:$E$20,"Diego")+COUNTIFS('S5'!$B$6:$B$20,$A104,'S5'!$E$6:$E$20,"Ambos")+COUNTIFS('S6'!$B$6:$B$17,$A104,'S6'!$E$6:$E$17,"Diego")+COUNTIFS('S6'!$B$6:$B$17,$A104,'S6'!$E$6:$E$17,"Ambos")+COUNTIFS('S7'!$B$6:$B$19,$A104,'S7'!$E$6:$E$19,"Diego")+COUNTIFS('S7'!$B$6:$B$19,$A104,'S7'!$E$6:$E$19,"Ambos")+COUNTIFS('S8'!$B$6:$B$23,$A104,'S8'!$E$6:$E$23,"Diego")+COUNTIFS('S8'!$B$6:$B$23,$A104,'S8'!$E$6:$E$23,"Ambos")+COUNTIFS('S9'!$B$6:$B$15,$A104,'S9'!$E$6:$E$15,"Diego")+COUNTIFS('S9'!$B$6:$B$15,$A104,'S9'!$E$6:$E$15,"Ambos")+COUNTIFS('S10'!$B$6:$B$13,$A104,'S10'!$E$6:$E$13,"Diego")+COUNTIFS('S10'!$B$6:$B$13,$A104,'S10'!$E$6:$E$13,"Ambos")+COUNTIFS('Holgura'!$B$6:$B$11,$A104,'Holgura'!$E$6:$E$11,"Diego")+COUNTIFS('Holgura'!$B$6:$B$11,$A104,'Holgura'!$E$6:$E$11,"Ambos")+COUNTIFS('Entrega'!$B$6:$B$9,$A104,'Entrega'!$E$6:$E$9,"Diego")+COUNTIFS('Entrega'!$B$6:$B$9,$A104,'Entrega'!$E$6:$E$9,"Ambos")+COUNTIFS('Defensa'!$B$6:$B$10,$A104,'Defensa'!$E$6:$E$10,"Diego")+COUNTIFS('Defensa'!$B$6:$B$10,$A104,'Defensa'!$E$6:$E$10,"Ambos")</f>
         <v/>
       </c>
     </row>
@@ -11580,19 +11601,19 @@
         <v/>
       </c>
       <c r="D105" s="21">
-        <f>SUMIFS('S1'!$I$6:$I$32,'S1'!$B$6:$B$32,$A105,'S1'!$E$6:$E$32,"Víctor")+SUMIFS('S1'!$I$6:$I$32,'S1'!$B$6:$B$32,$A105,'S1'!$E$6:$E$32,"Ambos")+SUMIFS('S2'!$I$6:$I$23,'S2'!$B$6:$B$23,$A105,'S2'!$E$6:$E$23,"Víctor")+SUMIFS('S2'!$I$6:$I$23,'S2'!$B$6:$B$23,$A105,'S2'!$E$6:$E$23,"Ambos")+SUMIFS('S3'!$I$6:$I$19,'S3'!$B$6:$B$19,$A105,'S3'!$E$6:$E$19,"Víctor")+SUMIFS('S3'!$I$6:$I$19,'S3'!$B$6:$B$19,$A105,'S3'!$E$6:$E$19,"Ambos")+SUMIFS('S4'!$I$6:$I$20,'S4'!$B$6:$B$20,$A105,'S4'!$E$6:$E$20,"Víctor")+SUMIFS('S4'!$I$6:$I$20,'S4'!$B$6:$B$20,$A105,'S4'!$E$6:$E$20,"Ambos")+SUMIFS('S5'!$I$6:$I$20,'S5'!$B$6:$B$20,$A105,'S5'!$E$6:$E$20,"Víctor")+SUMIFS('S5'!$I$6:$I$20,'S5'!$B$6:$B$20,$A105,'S5'!$E$6:$E$20,"Ambos")+SUMIFS('S6'!$I$6:$I$17,'S6'!$B$6:$B$17,$A105,'S6'!$E$6:$E$17,"Víctor")+SUMIFS('S6'!$I$6:$I$17,'S6'!$B$6:$B$17,$A105,'S6'!$E$6:$E$17,"Ambos")+SUMIFS('S7'!$I$6:$I$19,'S7'!$B$6:$B$19,$A105,'S7'!$E$6:$E$19,"Víctor")+SUMIFS('S7'!$I$6:$I$19,'S7'!$B$6:$B$19,$A105,'S7'!$E$6:$E$19,"Ambos")+SUMIFS('S8'!$I$6:$I$23,'S8'!$B$6:$B$23,$A105,'S8'!$E$6:$E$23,"Víctor")+SUMIFS('S8'!$I$6:$I$23,'S8'!$B$6:$B$23,$A105,'S8'!$E$6:$E$23,"Ambos")+SUMIFS('S9'!$I$6:$I$15,'S9'!$B$6:$B$15,$A105,'S9'!$E$6:$E$15,"Víctor")+SUMIFS('S9'!$I$6:$I$15,'S9'!$B$6:$B$15,$A105,'S9'!$E$6:$E$15,"Ambos")+SUMIFS('S10'!$I$6:$I$13,'S10'!$B$6:$B$13,$A105,'S10'!$E$6:$E$13,"Víctor")+SUMIFS('S10'!$I$6:$I$13,'S10'!$B$6:$B$13,$A105,'S10'!$E$6:$E$13,"Ambos")+SUMIFS('Holgura'!$I$6:$I$11,'Holgura'!$B$6:$B$11,$A105,'Holgura'!$E$6:$E$11,"Víctor")+SUMIFS('Holgura'!$I$6:$I$11,'Holgura'!$B$6:$B$11,$A105,'Holgura'!$E$6:$E$11,"Ambos")+SUMIFS('Entrega'!$I$6:$I$9,'Entrega'!$B$6:$B$9,$A105,'Entrega'!$E$6:$E$9,"Víctor")+SUMIFS('Entrega'!$I$6:$I$9,'Entrega'!$B$6:$B$9,$A105,'Entrega'!$E$6:$E$9,"Ambos")+SUMIFS('Defensa'!$I$6:$I$10,'Defensa'!$B$6:$B$10,$A105,'Defensa'!$E$6:$E$10,"Víctor")+SUMIFS('Defensa'!$I$6:$I$10,'Defensa'!$B$6:$B$10,$A105,'Defensa'!$E$6:$E$10,"Ambos")</f>
+        <f>SUMIFS('S1'!$I$6:$I$32,'S1'!$B$6:$B$32,$A105,'S1'!$E$6:$E$32,"Víctor")+SUMIFS('S1'!$I$6:$I$32,'S1'!$B$6:$B$32,$A105,'S1'!$E$6:$E$32,"Ambos")+SUMIFS('S2'!$I$6:$I$23,'S2'!$B$6:$B$23,$A105,'S2'!$E$6:$E$23,"Víctor")+SUMIFS('S2'!$I$6:$I$23,'S2'!$B$6:$B$23,$A105,'S2'!$E$6:$E$23,"Ambos")+SUMIFS('S3'!$I$6:$I$24,'S3'!$B$6:$B$24,$A105,'S3'!$E$6:$E$24,"Víctor")+SUMIFS('S3'!$I$6:$I$24,'S3'!$B$6:$B$24,$A105,'S3'!$E$6:$E$24,"Ambos")+SUMIFS('S4'!$I$6:$I$22,'S4'!$B$6:$B$22,$A105,'S4'!$E$6:$E$22,"Víctor")+SUMIFS('S4'!$I$6:$I$22,'S4'!$B$6:$B$22,$A105,'S4'!$E$6:$E$22,"Ambos")+SUMIFS('S5'!$I$6:$I$20,'S5'!$B$6:$B$20,$A105,'S5'!$E$6:$E$20,"Víctor")+SUMIFS('S5'!$I$6:$I$20,'S5'!$B$6:$B$20,$A105,'S5'!$E$6:$E$20,"Ambos")+SUMIFS('S6'!$I$6:$I$17,'S6'!$B$6:$B$17,$A105,'S6'!$E$6:$E$17,"Víctor")+SUMIFS('S6'!$I$6:$I$17,'S6'!$B$6:$B$17,$A105,'S6'!$E$6:$E$17,"Ambos")+SUMIFS('S7'!$I$6:$I$19,'S7'!$B$6:$B$19,$A105,'S7'!$E$6:$E$19,"Víctor")+SUMIFS('S7'!$I$6:$I$19,'S7'!$B$6:$B$19,$A105,'S7'!$E$6:$E$19,"Ambos")+SUMIFS('S8'!$I$6:$I$23,'S8'!$B$6:$B$23,$A105,'S8'!$E$6:$E$23,"Víctor")+SUMIFS('S8'!$I$6:$I$23,'S8'!$B$6:$B$23,$A105,'S8'!$E$6:$E$23,"Ambos")+SUMIFS('S9'!$I$6:$I$15,'S9'!$B$6:$B$15,$A105,'S9'!$E$6:$E$15,"Víctor")+SUMIFS('S9'!$I$6:$I$15,'S9'!$B$6:$B$15,$A105,'S9'!$E$6:$E$15,"Ambos")+SUMIFS('S10'!$I$6:$I$13,'S10'!$B$6:$B$13,$A105,'S10'!$E$6:$E$13,"Víctor")+SUMIFS('S10'!$I$6:$I$13,'S10'!$B$6:$B$13,$A105,'S10'!$E$6:$E$13,"Ambos")+SUMIFS('Holgura'!$I$6:$I$11,'Holgura'!$B$6:$B$11,$A105,'Holgura'!$E$6:$E$11,"Víctor")+SUMIFS('Holgura'!$I$6:$I$11,'Holgura'!$B$6:$B$11,$A105,'Holgura'!$E$6:$E$11,"Ambos")+SUMIFS('Entrega'!$I$6:$I$9,'Entrega'!$B$6:$B$9,$A105,'Entrega'!$E$6:$E$9,"Víctor")+SUMIFS('Entrega'!$I$6:$I$9,'Entrega'!$B$6:$B$9,$A105,'Entrega'!$E$6:$E$9,"Ambos")+SUMIFS('Defensa'!$I$6:$I$10,'Defensa'!$B$6:$B$10,$A105,'Defensa'!$E$6:$E$10,"Víctor")+SUMIFS('Defensa'!$I$6:$I$10,'Defensa'!$B$6:$B$10,$A105,'Defensa'!$E$6:$E$10,"Ambos")</f>
         <v/>
       </c>
       <c r="E105" s="21">
-        <f>SUMIFS('S1'!$I$6:$I$32,'S1'!$B$6:$B$32,$A105,'S1'!$E$6:$E$32,"Diego")+SUMIFS('S1'!$I$6:$I$32,'S1'!$B$6:$B$32,$A105,'S1'!$E$6:$E$32,"Ambos")+SUMIFS('S2'!$I$6:$I$23,'S2'!$B$6:$B$23,$A105,'S2'!$E$6:$E$23,"Diego")+SUMIFS('S2'!$I$6:$I$23,'S2'!$B$6:$B$23,$A105,'S2'!$E$6:$E$23,"Ambos")+SUMIFS('S3'!$I$6:$I$19,'S3'!$B$6:$B$19,$A105,'S3'!$E$6:$E$19,"Diego")+SUMIFS('S3'!$I$6:$I$19,'S3'!$B$6:$B$19,$A105,'S3'!$E$6:$E$19,"Ambos")+SUMIFS('S4'!$I$6:$I$20,'S4'!$B$6:$B$20,$A105,'S4'!$E$6:$E$20,"Diego")+SUMIFS('S4'!$I$6:$I$20,'S4'!$B$6:$B$20,$A105,'S4'!$E$6:$E$20,"Ambos")+SUMIFS('S5'!$I$6:$I$20,'S5'!$B$6:$B$20,$A105,'S5'!$E$6:$E$20,"Diego")+SUMIFS('S5'!$I$6:$I$20,'S5'!$B$6:$B$20,$A105,'S5'!$E$6:$E$20,"Ambos")+SUMIFS('S6'!$I$6:$I$17,'S6'!$B$6:$B$17,$A105,'S6'!$E$6:$E$17,"Diego")+SUMIFS('S6'!$I$6:$I$17,'S6'!$B$6:$B$17,$A105,'S6'!$E$6:$E$17,"Ambos")+SUMIFS('S7'!$I$6:$I$19,'S7'!$B$6:$B$19,$A105,'S7'!$E$6:$E$19,"Diego")+SUMIFS('S7'!$I$6:$I$19,'S7'!$B$6:$B$19,$A105,'S7'!$E$6:$E$19,"Ambos")+SUMIFS('S8'!$I$6:$I$23,'S8'!$B$6:$B$23,$A105,'S8'!$E$6:$E$23,"Diego")+SUMIFS('S8'!$I$6:$I$23,'S8'!$B$6:$B$23,$A105,'S8'!$E$6:$E$23,"Ambos")+SUMIFS('S9'!$I$6:$I$15,'S9'!$B$6:$B$15,$A105,'S9'!$E$6:$E$15,"Diego")+SUMIFS('S9'!$I$6:$I$15,'S9'!$B$6:$B$15,$A105,'S9'!$E$6:$E$15,"Ambos")+SUMIFS('S10'!$I$6:$I$13,'S10'!$B$6:$B$13,$A105,'S10'!$E$6:$E$13,"Diego")+SUMIFS('S10'!$I$6:$I$13,'S10'!$B$6:$B$13,$A105,'S10'!$E$6:$E$13,"Ambos")+SUMIFS('Holgura'!$I$6:$I$11,'Holgura'!$B$6:$B$11,$A105,'Holgura'!$E$6:$E$11,"Diego")+SUMIFS('Holgura'!$I$6:$I$11,'Holgura'!$B$6:$B$11,$A105,'Holgura'!$E$6:$E$11,"Ambos")+SUMIFS('Entrega'!$I$6:$I$9,'Entrega'!$B$6:$B$9,$A105,'Entrega'!$E$6:$E$9,"Diego")+SUMIFS('Entrega'!$I$6:$I$9,'Entrega'!$B$6:$B$9,$A105,'Entrega'!$E$6:$E$9,"Ambos")+SUMIFS('Defensa'!$I$6:$I$10,'Defensa'!$B$6:$B$10,$A105,'Defensa'!$E$6:$E$10,"Diego")+SUMIFS('Defensa'!$I$6:$I$10,'Defensa'!$B$6:$B$10,$A105,'Defensa'!$E$6:$E$10,"Ambos")</f>
+        <f>SUMIFS('S1'!$I$6:$I$32,'S1'!$B$6:$B$32,$A105,'S1'!$E$6:$E$32,"Diego")+SUMIFS('S1'!$I$6:$I$32,'S1'!$B$6:$B$32,$A105,'S1'!$E$6:$E$32,"Ambos")+SUMIFS('S2'!$I$6:$I$23,'S2'!$B$6:$B$23,$A105,'S2'!$E$6:$E$23,"Diego")+SUMIFS('S2'!$I$6:$I$23,'S2'!$B$6:$B$23,$A105,'S2'!$E$6:$E$23,"Ambos")+SUMIFS('S3'!$I$6:$I$24,'S3'!$B$6:$B$24,$A105,'S3'!$E$6:$E$24,"Diego")+SUMIFS('S3'!$I$6:$I$24,'S3'!$B$6:$B$24,$A105,'S3'!$E$6:$E$24,"Ambos")+SUMIFS('S4'!$I$6:$I$22,'S4'!$B$6:$B$22,$A105,'S4'!$E$6:$E$22,"Diego")+SUMIFS('S4'!$I$6:$I$22,'S4'!$B$6:$B$22,$A105,'S4'!$E$6:$E$22,"Ambos")+SUMIFS('S5'!$I$6:$I$20,'S5'!$B$6:$B$20,$A105,'S5'!$E$6:$E$20,"Diego")+SUMIFS('S5'!$I$6:$I$20,'S5'!$B$6:$B$20,$A105,'S5'!$E$6:$E$20,"Ambos")+SUMIFS('S6'!$I$6:$I$17,'S6'!$B$6:$B$17,$A105,'S6'!$E$6:$E$17,"Diego")+SUMIFS('S6'!$I$6:$I$17,'S6'!$B$6:$B$17,$A105,'S6'!$E$6:$E$17,"Ambos")+SUMIFS('S7'!$I$6:$I$19,'S7'!$B$6:$B$19,$A105,'S7'!$E$6:$E$19,"Diego")+SUMIFS('S7'!$I$6:$I$19,'S7'!$B$6:$B$19,$A105,'S7'!$E$6:$E$19,"Ambos")+SUMIFS('S8'!$I$6:$I$23,'S8'!$B$6:$B$23,$A105,'S8'!$E$6:$E$23,"Diego")+SUMIFS('S8'!$I$6:$I$23,'S8'!$B$6:$B$23,$A105,'S8'!$E$6:$E$23,"Ambos")+SUMIFS('S9'!$I$6:$I$15,'S9'!$B$6:$B$15,$A105,'S9'!$E$6:$E$15,"Diego")+SUMIFS('S9'!$I$6:$I$15,'S9'!$B$6:$B$15,$A105,'S9'!$E$6:$E$15,"Ambos")+SUMIFS('S10'!$I$6:$I$13,'S10'!$B$6:$B$13,$A105,'S10'!$E$6:$E$13,"Diego")+SUMIFS('S10'!$I$6:$I$13,'S10'!$B$6:$B$13,$A105,'S10'!$E$6:$E$13,"Ambos")+SUMIFS('Holgura'!$I$6:$I$11,'Holgura'!$B$6:$B$11,$A105,'Holgura'!$E$6:$E$11,"Diego")+SUMIFS('Holgura'!$I$6:$I$11,'Holgura'!$B$6:$B$11,$A105,'Holgura'!$E$6:$E$11,"Ambos")+SUMIFS('Entrega'!$I$6:$I$9,'Entrega'!$B$6:$B$9,$A105,'Entrega'!$E$6:$E$9,"Diego")+SUMIFS('Entrega'!$I$6:$I$9,'Entrega'!$B$6:$B$9,$A105,'Entrega'!$E$6:$E$9,"Ambos")+SUMIFS('Defensa'!$I$6:$I$10,'Defensa'!$B$6:$B$10,$A105,'Defensa'!$E$6:$E$10,"Diego")+SUMIFS('Defensa'!$I$6:$I$10,'Defensa'!$B$6:$B$10,$A105,'Defensa'!$E$6:$E$10,"Ambos")</f>
         <v/>
       </c>
       <c r="F105" s="21">
-        <f>COUNTIFS('S1'!$B$6:$B$32,$A105,'S1'!$E$6:$E$32,"Víctor")+COUNTIFS('S1'!$B$6:$B$32,$A105,'S1'!$E$6:$E$32,"Ambos")+COUNTIFS('S2'!$B$6:$B$23,$A105,'S2'!$E$6:$E$23,"Víctor")+COUNTIFS('S2'!$B$6:$B$23,$A105,'S2'!$E$6:$E$23,"Ambos")+COUNTIFS('S3'!$B$6:$B$19,$A105,'S3'!$E$6:$E$19,"Víctor")+COUNTIFS('S3'!$B$6:$B$19,$A105,'S3'!$E$6:$E$19,"Ambos")+COUNTIFS('S4'!$B$6:$B$20,$A105,'S4'!$E$6:$E$20,"Víctor")+COUNTIFS('S4'!$B$6:$B$20,$A105,'S4'!$E$6:$E$20,"Ambos")+COUNTIFS('S5'!$B$6:$B$20,$A105,'S5'!$E$6:$E$20,"Víctor")+COUNTIFS('S5'!$B$6:$B$20,$A105,'S5'!$E$6:$E$20,"Ambos")+COUNTIFS('S6'!$B$6:$B$17,$A105,'S6'!$E$6:$E$17,"Víctor")+COUNTIFS('S6'!$B$6:$B$17,$A105,'S6'!$E$6:$E$17,"Ambos")+COUNTIFS('S7'!$B$6:$B$19,$A105,'S7'!$E$6:$E$19,"Víctor")+COUNTIFS('S7'!$B$6:$B$19,$A105,'S7'!$E$6:$E$19,"Ambos")+COUNTIFS('S8'!$B$6:$B$23,$A105,'S8'!$E$6:$E$23,"Víctor")+COUNTIFS('S8'!$B$6:$B$23,$A105,'S8'!$E$6:$E$23,"Ambos")+COUNTIFS('S9'!$B$6:$B$15,$A105,'S9'!$E$6:$E$15,"Víctor")+COUNTIFS('S9'!$B$6:$B$15,$A105,'S9'!$E$6:$E$15,"Ambos")+COUNTIFS('S10'!$B$6:$B$13,$A105,'S10'!$E$6:$E$13,"Víctor")+COUNTIFS('S10'!$B$6:$B$13,$A105,'S10'!$E$6:$E$13,"Ambos")+COUNTIFS('Holgura'!$B$6:$B$11,$A105,'Holgura'!$E$6:$E$11,"Víctor")+COUNTIFS('Holgura'!$B$6:$B$11,$A105,'Holgura'!$E$6:$E$11,"Ambos")+COUNTIFS('Entrega'!$B$6:$B$9,$A105,'Entrega'!$E$6:$E$9,"Víctor")+COUNTIFS('Entrega'!$B$6:$B$9,$A105,'Entrega'!$E$6:$E$9,"Ambos")+COUNTIFS('Defensa'!$B$6:$B$10,$A105,'Defensa'!$E$6:$E$10,"Víctor")+COUNTIFS('Defensa'!$B$6:$B$10,$A105,'Defensa'!$E$6:$E$10,"Ambos")</f>
+        <f>COUNTIFS('S1'!$B$6:$B$32,$A105,'S1'!$E$6:$E$32,"Víctor")+COUNTIFS('S1'!$B$6:$B$32,$A105,'S1'!$E$6:$E$32,"Ambos")+COUNTIFS('S2'!$B$6:$B$23,$A105,'S2'!$E$6:$E$23,"Víctor")+COUNTIFS('S2'!$B$6:$B$23,$A105,'S2'!$E$6:$E$23,"Ambos")+COUNTIFS('S3'!$B$6:$B$24,$A105,'S3'!$E$6:$E$24,"Víctor")+COUNTIFS('S3'!$B$6:$B$24,$A105,'S3'!$E$6:$E$24,"Ambos")+COUNTIFS('S4'!$B$6:$B$22,$A105,'S4'!$E$6:$E$22,"Víctor")+COUNTIFS('S4'!$B$6:$B$22,$A105,'S4'!$E$6:$E$22,"Ambos")+COUNTIFS('S5'!$B$6:$B$20,$A105,'S5'!$E$6:$E$20,"Víctor")+COUNTIFS('S5'!$B$6:$B$20,$A105,'S5'!$E$6:$E$20,"Ambos")+COUNTIFS('S6'!$B$6:$B$17,$A105,'S6'!$E$6:$E$17,"Víctor")+COUNTIFS('S6'!$B$6:$B$17,$A105,'S6'!$E$6:$E$17,"Ambos")+COUNTIFS('S7'!$B$6:$B$19,$A105,'S7'!$E$6:$E$19,"Víctor")+COUNTIFS('S7'!$B$6:$B$19,$A105,'S7'!$E$6:$E$19,"Ambos")+COUNTIFS('S8'!$B$6:$B$23,$A105,'S8'!$E$6:$E$23,"Víctor")+COUNTIFS('S8'!$B$6:$B$23,$A105,'S8'!$E$6:$E$23,"Ambos")+COUNTIFS('S9'!$B$6:$B$15,$A105,'S9'!$E$6:$E$15,"Víctor")+COUNTIFS('S9'!$B$6:$B$15,$A105,'S9'!$E$6:$E$15,"Ambos")+COUNTIFS('S10'!$B$6:$B$13,$A105,'S10'!$E$6:$E$13,"Víctor")+COUNTIFS('S10'!$B$6:$B$13,$A105,'S10'!$E$6:$E$13,"Ambos")+COUNTIFS('Holgura'!$B$6:$B$11,$A105,'Holgura'!$E$6:$E$11,"Víctor")+COUNTIFS('Holgura'!$B$6:$B$11,$A105,'Holgura'!$E$6:$E$11,"Ambos")+COUNTIFS('Entrega'!$B$6:$B$9,$A105,'Entrega'!$E$6:$E$9,"Víctor")+COUNTIFS('Entrega'!$B$6:$B$9,$A105,'Entrega'!$E$6:$E$9,"Ambos")+COUNTIFS('Defensa'!$B$6:$B$10,$A105,'Defensa'!$E$6:$E$10,"Víctor")+COUNTIFS('Defensa'!$B$6:$B$10,$A105,'Defensa'!$E$6:$E$10,"Ambos")</f>
         <v/>
       </c>
       <c r="G105" s="21">
-        <f>COUNTIFS('S1'!$B$6:$B$32,$A105,'S1'!$E$6:$E$32,"Diego")+COUNTIFS('S1'!$B$6:$B$32,$A105,'S1'!$E$6:$E$32,"Ambos")+COUNTIFS('S2'!$B$6:$B$23,$A105,'S2'!$E$6:$E$23,"Diego")+COUNTIFS('S2'!$B$6:$B$23,$A105,'S2'!$E$6:$E$23,"Ambos")+COUNTIFS('S3'!$B$6:$B$19,$A105,'S3'!$E$6:$E$19,"Diego")+COUNTIFS('S3'!$B$6:$B$19,$A105,'S3'!$E$6:$E$19,"Ambos")+COUNTIFS('S4'!$B$6:$B$20,$A105,'S4'!$E$6:$E$20,"Diego")+COUNTIFS('S4'!$B$6:$B$20,$A105,'S4'!$E$6:$E$20,"Ambos")+COUNTIFS('S5'!$B$6:$B$20,$A105,'S5'!$E$6:$E$20,"Diego")+COUNTIFS('S5'!$B$6:$B$20,$A105,'S5'!$E$6:$E$20,"Ambos")+COUNTIFS('S6'!$B$6:$B$17,$A105,'S6'!$E$6:$E$17,"Diego")+COUNTIFS('S6'!$B$6:$B$17,$A105,'S6'!$E$6:$E$17,"Ambos")+COUNTIFS('S7'!$B$6:$B$19,$A105,'S7'!$E$6:$E$19,"Diego")+COUNTIFS('S7'!$B$6:$B$19,$A105,'S7'!$E$6:$E$19,"Ambos")+COUNTIFS('S8'!$B$6:$B$23,$A105,'S8'!$E$6:$E$23,"Diego")+COUNTIFS('S8'!$B$6:$B$23,$A105,'S8'!$E$6:$E$23,"Ambos")+COUNTIFS('S9'!$B$6:$B$15,$A105,'S9'!$E$6:$E$15,"Diego")+COUNTIFS('S9'!$B$6:$B$15,$A105,'S9'!$E$6:$E$15,"Ambos")+COUNTIFS('S10'!$B$6:$B$13,$A105,'S10'!$E$6:$E$13,"Diego")+COUNTIFS('S10'!$B$6:$B$13,$A105,'S10'!$E$6:$E$13,"Ambos")+COUNTIFS('Holgura'!$B$6:$B$11,$A105,'Holgura'!$E$6:$E$11,"Diego")+COUNTIFS('Holgura'!$B$6:$B$11,$A105,'Holgura'!$E$6:$E$11,"Ambos")+COUNTIFS('Entrega'!$B$6:$B$9,$A105,'Entrega'!$E$6:$E$9,"Diego")+COUNTIFS('Entrega'!$B$6:$B$9,$A105,'Entrega'!$E$6:$E$9,"Ambos")+COUNTIFS('Defensa'!$B$6:$B$10,$A105,'Defensa'!$E$6:$E$10,"Diego")+COUNTIFS('Defensa'!$B$6:$B$10,$A105,'Defensa'!$E$6:$E$10,"Ambos")</f>
+        <f>COUNTIFS('S1'!$B$6:$B$32,$A105,'S1'!$E$6:$E$32,"Diego")+COUNTIFS('S1'!$B$6:$B$32,$A105,'S1'!$E$6:$E$32,"Ambos")+COUNTIFS('S2'!$B$6:$B$23,$A105,'S2'!$E$6:$E$23,"Diego")+COUNTIFS('S2'!$B$6:$B$23,$A105,'S2'!$E$6:$E$23,"Ambos")+COUNTIFS('S3'!$B$6:$B$24,$A105,'S3'!$E$6:$E$24,"Diego")+COUNTIFS('S3'!$B$6:$B$24,$A105,'S3'!$E$6:$E$24,"Ambos")+COUNTIFS('S4'!$B$6:$B$22,$A105,'S4'!$E$6:$E$22,"Diego")+COUNTIFS('S4'!$B$6:$B$22,$A105,'S4'!$E$6:$E$22,"Ambos")+COUNTIFS('S5'!$B$6:$B$20,$A105,'S5'!$E$6:$E$20,"Diego")+COUNTIFS('S5'!$B$6:$B$20,$A105,'S5'!$E$6:$E$20,"Ambos")+COUNTIFS('S6'!$B$6:$B$17,$A105,'S6'!$E$6:$E$17,"Diego")+COUNTIFS('S6'!$B$6:$B$17,$A105,'S6'!$E$6:$E$17,"Ambos")+COUNTIFS('S7'!$B$6:$B$19,$A105,'S7'!$E$6:$E$19,"Diego")+COUNTIFS('S7'!$B$6:$B$19,$A105,'S7'!$E$6:$E$19,"Ambos")+COUNTIFS('S8'!$B$6:$B$23,$A105,'S8'!$E$6:$E$23,"Diego")+COUNTIFS('S8'!$B$6:$B$23,$A105,'S8'!$E$6:$E$23,"Ambos")+COUNTIFS('S9'!$B$6:$B$15,$A105,'S9'!$E$6:$E$15,"Diego")+COUNTIFS('S9'!$B$6:$B$15,$A105,'S9'!$E$6:$E$15,"Ambos")+COUNTIFS('S10'!$B$6:$B$13,$A105,'S10'!$E$6:$E$13,"Diego")+COUNTIFS('S10'!$B$6:$B$13,$A105,'S10'!$E$6:$E$13,"Ambos")+COUNTIFS('Holgura'!$B$6:$B$11,$A105,'Holgura'!$E$6:$E$11,"Diego")+COUNTIFS('Holgura'!$B$6:$B$11,$A105,'Holgura'!$E$6:$E$11,"Ambos")+COUNTIFS('Entrega'!$B$6:$B$9,$A105,'Entrega'!$E$6:$E$9,"Diego")+COUNTIFS('Entrega'!$B$6:$B$9,$A105,'Entrega'!$E$6:$E$9,"Ambos")+COUNTIFS('Defensa'!$B$6:$B$10,$A105,'Defensa'!$E$6:$E$10,"Diego")+COUNTIFS('Defensa'!$B$6:$B$10,$A105,'Defensa'!$E$6:$E$10,"Ambos")</f>
         <v/>
       </c>
     </row>
@@ -11609,19 +11630,19 @@
         <v/>
       </c>
       <c r="D106" s="21">
-        <f>SUMIFS('S1'!$I$6:$I$32,'S1'!$B$6:$B$32,$A106,'S1'!$E$6:$E$32,"Víctor")+SUMIFS('S1'!$I$6:$I$32,'S1'!$B$6:$B$32,$A106,'S1'!$E$6:$E$32,"Ambos")+SUMIFS('S2'!$I$6:$I$23,'S2'!$B$6:$B$23,$A106,'S2'!$E$6:$E$23,"Víctor")+SUMIFS('S2'!$I$6:$I$23,'S2'!$B$6:$B$23,$A106,'S2'!$E$6:$E$23,"Ambos")+SUMIFS('S3'!$I$6:$I$19,'S3'!$B$6:$B$19,$A106,'S3'!$E$6:$E$19,"Víctor")+SUMIFS('S3'!$I$6:$I$19,'S3'!$B$6:$B$19,$A106,'S3'!$E$6:$E$19,"Ambos")+SUMIFS('S4'!$I$6:$I$20,'S4'!$B$6:$B$20,$A106,'S4'!$E$6:$E$20,"Víctor")+SUMIFS('S4'!$I$6:$I$20,'S4'!$B$6:$B$20,$A106,'S4'!$E$6:$E$20,"Ambos")+SUMIFS('S5'!$I$6:$I$20,'S5'!$B$6:$B$20,$A106,'S5'!$E$6:$E$20,"Víctor")+SUMIFS('S5'!$I$6:$I$20,'S5'!$B$6:$B$20,$A106,'S5'!$E$6:$E$20,"Ambos")+SUMIFS('S6'!$I$6:$I$17,'S6'!$B$6:$B$17,$A106,'S6'!$E$6:$E$17,"Víctor")+SUMIFS('S6'!$I$6:$I$17,'S6'!$B$6:$B$17,$A106,'S6'!$E$6:$E$17,"Ambos")+SUMIFS('S7'!$I$6:$I$19,'S7'!$B$6:$B$19,$A106,'S7'!$E$6:$E$19,"Víctor")+SUMIFS('S7'!$I$6:$I$19,'S7'!$B$6:$B$19,$A106,'S7'!$E$6:$E$19,"Ambos")+SUMIFS('S8'!$I$6:$I$23,'S8'!$B$6:$B$23,$A106,'S8'!$E$6:$E$23,"Víctor")+SUMIFS('S8'!$I$6:$I$23,'S8'!$B$6:$B$23,$A106,'S8'!$E$6:$E$23,"Ambos")+SUMIFS('S9'!$I$6:$I$15,'S9'!$B$6:$B$15,$A106,'S9'!$E$6:$E$15,"Víctor")+SUMIFS('S9'!$I$6:$I$15,'S9'!$B$6:$B$15,$A106,'S9'!$E$6:$E$15,"Ambos")+SUMIFS('S10'!$I$6:$I$13,'S10'!$B$6:$B$13,$A106,'S10'!$E$6:$E$13,"Víctor")+SUMIFS('S10'!$I$6:$I$13,'S10'!$B$6:$B$13,$A106,'S10'!$E$6:$E$13,"Ambos")+SUMIFS('Holgura'!$I$6:$I$11,'Holgura'!$B$6:$B$11,$A106,'Holgura'!$E$6:$E$11,"Víctor")+SUMIFS('Holgura'!$I$6:$I$11,'Holgura'!$B$6:$B$11,$A106,'Holgura'!$E$6:$E$11,"Ambos")+SUMIFS('Entrega'!$I$6:$I$9,'Entrega'!$B$6:$B$9,$A106,'Entrega'!$E$6:$E$9,"Víctor")+SUMIFS('Entrega'!$I$6:$I$9,'Entrega'!$B$6:$B$9,$A106,'Entrega'!$E$6:$E$9,"Ambos")+SUMIFS('Defensa'!$I$6:$I$10,'Defensa'!$B$6:$B$10,$A106,'Defensa'!$E$6:$E$10,"Víctor")+SUMIFS('Defensa'!$I$6:$I$10,'Defensa'!$B$6:$B$10,$A106,'Defensa'!$E$6:$E$10,"Ambos")</f>
+        <f>SUMIFS('S1'!$I$6:$I$32,'S1'!$B$6:$B$32,$A106,'S1'!$E$6:$E$32,"Víctor")+SUMIFS('S1'!$I$6:$I$32,'S1'!$B$6:$B$32,$A106,'S1'!$E$6:$E$32,"Ambos")+SUMIFS('S2'!$I$6:$I$23,'S2'!$B$6:$B$23,$A106,'S2'!$E$6:$E$23,"Víctor")+SUMIFS('S2'!$I$6:$I$23,'S2'!$B$6:$B$23,$A106,'S2'!$E$6:$E$23,"Ambos")+SUMIFS('S3'!$I$6:$I$24,'S3'!$B$6:$B$24,$A106,'S3'!$E$6:$E$24,"Víctor")+SUMIFS('S3'!$I$6:$I$24,'S3'!$B$6:$B$24,$A106,'S3'!$E$6:$E$24,"Ambos")+SUMIFS('S4'!$I$6:$I$22,'S4'!$B$6:$B$22,$A106,'S4'!$E$6:$E$22,"Víctor")+SUMIFS('S4'!$I$6:$I$22,'S4'!$B$6:$B$22,$A106,'S4'!$E$6:$E$22,"Ambos")+SUMIFS('S5'!$I$6:$I$20,'S5'!$B$6:$B$20,$A106,'S5'!$E$6:$E$20,"Víctor")+SUMIFS('S5'!$I$6:$I$20,'S5'!$B$6:$B$20,$A106,'S5'!$E$6:$E$20,"Ambos")+SUMIFS('S6'!$I$6:$I$17,'S6'!$B$6:$B$17,$A106,'S6'!$E$6:$E$17,"Víctor")+SUMIFS('S6'!$I$6:$I$17,'S6'!$B$6:$B$17,$A106,'S6'!$E$6:$E$17,"Ambos")+SUMIFS('S7'!$I$6:$I$19,'S7'!$B$6:$B$19,$A106,'S7'!$E$6:$E$19,"Víctor")+SUMIFS('S7'!$I$6:$I$19,'S7'!$B$6:$B$19,$A106,'S7'!$E$6:$E$19,"Ambos")+SUMIFS('S8'!$I$6:$I$23,'S8'!$B$6:$B$23,$A106,'S8'!$E$6:$E$23,"Víctor")+SUMIFS('S8'!$I$6:$I$23,'S8'!$B$6:$B$23,$A106,'S8'!$E$6:$E$23,"Ambos")+SUMIFS('S9'!$I$6:$I$15,'S9'!$B$6:$B$15,$A106,'S9'!$E$6:$E$15,"Víctor")+SUMIFS('S9'!$I$6:$I$15,'S9'!$B$6:$B$15,$A106,'S9'!$E$6:$E$15,"Ambos")+SUMIFS('S10'!$I$6:$I$13,'S10'!$B$6:$B$13,$A106,'S10'!$E$6:$E$13,"Víctor")+SUMIFS('S10'!$I$6:$I$13,'S10'!$B$6:$B$13,$A106,'S10'!$E$6:$E$13,"Ambos")+SUMIFS('Holgura'!$I$6:$I$11,'Holgura'!$B$6:$B$11,$A106,'Holgura'!$E$6:$E$11,"Víctor")+SUMIFS('Holgura'!$I$6:$I$11,'Holgura'!$B$6:$B$11,$A106,'Holgura'!$E$6:$E$11,"Ambos")+SUMIFS('Entrega'!$I$6:$I$9,'Entrega'!$B$6:$B$9,$A106,'Entrega'!$E$6:$E$9,"Víctor")+SUMIFS('Entrega'!$I$6:$I$9,'Entrega'!$B$6:$B$9,$A106,'Entrega'!$E$6:$E$9,"Ambos")+SUMIFS('Defensa'!$I$6:$I$10,'Defensa'!$B$6:$B$10,$A106,'Defensa'!$E$6:$E$10,"Víctor")+SUMIFS('Defensa'!$I$6:$I$10,'Defensa'!$B$6:$B$10,$A106,'Defensa'!$E$6:$E$10,"Ambos")</f>
         <v/>
       </c>
       <c r="E106" s="21">
-        <f>SUMIFS('S1'!$I$6:$I$32,'S1'!$B$6:$B$32,$A106,'S1'!$E$6:$E$32,"Diego")+SUMIFS('S1'!$I$6:$I$32,'S1'!$B$6:$B$32,$A106,'S1'!$E$6:$E$32,"Ambos")+SUMIFS('S2'!$I$6:$I$23,'S2'!$B$6:$B$23,$A106,'S2'!$E$6:$E$23,"Diego")+SUMIFS('S2'!$I$6:$I$23,'S2'!$B$6:$B$23,$A106,'S2'!$E$6:$E$23,"Ambos")+SUMIFS('S3'!$I$6:$I$19,'S3'!$B$6:$B$19,$A106,'S3'!$E$6:$E$19,"Diego")+SUMIFS('S3'!$I$6:$I$19,'S3'!$B$6:$B$19,$A106,'S3'!$E$6:$E$19,"Ambos")+SUMIFS('S4'!$I$6:$I$20,'S4'!$B$6:$B$20,$A106,'S4'!$E$6:$E$20,"Diego")+SUMIFS('S4'!$I$6:$I$20,'S4'!$B$6:$B$20,$A106,'S4'!$E$6:$E$20,"Ambos")+SUMIFS('S5'!$I$6:$I$20,'S5'!$B$6:$B$20,$A106,'S5'!$E$6:$E$20,"Diego")+SUMIFS('S5'!$I$6:$I$20,'S5'!$B$6:$B$20,$A106,'S5'!$E$6:$E$20,"Ambos")+SUMIFS('S6'!$I$6:$I$17,'S6'!$B$6:$B$17,$A106,'S6'!$E$6:$E$17,"Diego")+SUMIFS('S6'!$I$6:$I$17,'S6'!$B$6:$B$17,$A106,'S6'!$E$6:$E$17,"Ambos")+SUMIFS('S7'!$I$6:$I$19,'S7'!$B$6:$B$19,$A106,'S7'!$E$6:$E$19,"Diego")+SUMIFS('S7'!$I$6:$I$19,'S7'!$B$6:$B$19,$A106,'S7'!$E$6:$E$19,"Ambos")+SUMIFS('S8'!$I$6:$I$23,'S8'!$B$6:$B$23,$A106,'S8'!$E$6:$E$23,"Diego")+SUMIFS('S8'!$I$6:$I$23,'S8'!$B$6:$B$23,$A106,'S8'!$E$6:$E$23,"Ambos")+SUMIFS('S9'!$I$6:$I$15,'S9'!$B$6:$B$15,$A106,'S9'!$E$6:$E$15,"Diego")+SUMIFS('S9'!$I$6:$I$15,'S9'!$B$6:$B$15,$A106,'S9'!$E$6:$E$15,"Ambos")+SUMIFS('S10'!$I$6:$I$13,'S10'!$B$6:$B$13,$A106,'S10'!$E$6:$E$13,"Diego")+SUMIFS('S10'!$I$6:$I$13,'S10'!$B$6:$B$13,$A106,'S10'!$E$6:$E$13,"Ambos")+SUMIFS('Holgura'!$I$6:$I$11,'Holgura'!$B$6:$B$11,$A106,'Holgura'!$E$6:$E$11,"Diego")+SUMIFS('Holgura'!$I$6:$I$11,'Holgura'!$B$6:$B$11,$A106,'Holgura'!$E$6:$E$11,"Ambos")+SUMIFS('Entrega'!$I$6:$I$9,'Entrega'!$B$6:$B$9,$A106,'Entrega'!$E$6:$E$9,"Diego")+SUMIFS('Entrega'!$I$6:$I$9,'Entrega'!$B$6:$B$9,$A106,'Entrega'!$E$6:$E$9,"Ambos")+SUMIFS('Defensa'!$I$6:$I$10,'Defensa'!$B$6:$B$10,$A106,'Defensa'!$E$6:$E$10,"Diego")+SUMIFS('Defensa'!$I$6:$I$10,'Defensa'!$B$6:$B$10,$A106,'Defensa'!$E$6:$E$10,"Ambos")</f>
+        <f>SUMIFS('S1'!$I$6:$I$32,'S1'!$B$6:$B$32,$A106,'S1'!$E$6:$E$32,"Diego")+SUMIFS('S1'!$I$6:$I$32,'S1'!$B$6:$B$32,$A106,'S1'!$E$6:$E$32,"Ambos")+SUMIFS('S2'!$I$6:$I$23,'S2'!$B$6:$B$23,$A106,'S2'!$E$6:$E$23,"Diego")+SUMIFS('S2'!$I$6:$I$23,'S2'!$B$6:$B$23,$A106,'S2'!$E$6:$E$23,"Ambos")+SUMIFS('S3'!$I$6:$I$24,'S3'!$B$6:$B$24,$A106,'S3'!$E$6:$E$24,"Diego")+SUMIFS('S3'!$I$6:$I$24,'S3'!$B$6:$B$24,$A106,'S3'!$E$6:$E$24,"Ambos")+SUMIFS('S4'!$I$6:$I$22,'S4'!$B$6:$B$22,$A106,'S4'!$E$6:$E$22,"Diego")+SUMIFS('S4'!$I$6:$I$22,'S4'!$B$6:$B$22,$A106,'S4'!$E$6:$E$22,"Ambos")+SUMIFS('S5'!$I$6:$I$20,'S5'!$B$6:$B$20,$A106,'S5'!$E$6:$E$20,"Diego")+SUMIFS('S5'!$I$6:$I$20,'S5'!$B$6:$B$20,$A106,'S5'!$E$6:$E$20,"Ambos")+SUMIFS('S6'!$I$6:$I$17,'S6'!$B$6:$B$17,$A106,'S6'!$E$6:$E$17,"Diego")+SUMIFS('S6'!$I$6:$I$17,'S6'!$B$6:$B$17,$A106,'S6'!$E$6:$E$17,"Ambos")+SUMIFS('S7'!$I$6:$I$19,'S7'!$B$6:$B$19,$A106,'S7'!$E$6:$E$19,"Diego")+SUMIFS('S7'!$I$6:$I$19,'S7'!$B$6:$B$19,$A106,'S7'!$E$6:$E$19,"Ambos")+SUMIFS('S8'!$I$6:$I$23,'S8'!$B$6:$B$23,$A106,'S8'!$E$6:$E$23,"Diego")+SUMIFS('S8'!$I$6:$I$23,'S8'!$B$6:$B$23,$A106,'S8'!$E$6:$E$23,"Ambos")+SUMIFS('S9'!$I$6:$I$15,'S9'!$B$6:$B$15,$A106,'S9'!$E$6:$E$15,"Diego")+SUMIFS('S9'!$I$6:$I$15,'S9'!$B$6:$B$15,$A106,'S9'!$E$6:$E$15,"Ambos")+SUMIFS('S10'!$I$6:$I$13,'S10'!$B$6:$B$13,$A106,'S10'!$E$6:$E$13,"Diego")+SUMIFS('S10'!$I$6:$I$13,'S10'!$B$6:$B$13,$A106,'S10'!$E$6:$E$13,"Ambos")+SUMIFS('Holgura'!$I$6:$I$11,'Holgura'!$B$6:$B$11,$A106,'Holgura'!$E$6:$E$11,"Diego")+SUMIFS('Holgura'!$I$6:$I$11,'Holgura'!$B$6:$B$11,$A106,'Holgura'!$E$6:$E$11,"Ambos")+SUMIFS('Entrega'!$I$6:$I$9,'Entrega'!$B$6:$B$9,$A106,'Entrega'!$E$6:$E$9,"Diego")+SUMIFS('Entrega'!$I$6:$I$9,'Entrega'!$B$6:$B$9,$A106,'Entrega'!$E$6:$E$9,"Ambos")+SUMIFS('Defensa'!$I$6:$I$10,'Defensa'!$B$6:$B$10,$A106,'Defensa'!$E$6:$E$10,"Diego")+SUMIFS('Defensa'!$I$6:$I$10,'Defensa'!$B$6:$B$10,$A106,'Defensa'!$E$6:$E$10,"Ambos")</f>
         <v/>
       </c>
       <c r="F106" s="21">
-        <f>COUNTIFS('S1'!$B$6:$B$32,$A106,'S1'!$E$6:$E$32,"Víctor")+COUNTIFS('S1'!$B$6:$B$32,$A106,'S1'!$E$6:$E$32,"Ambos")+COUNTIFS('S2'!$B$6:$B$23,$A106,'S2'!$E$6:$E$23,"Víctor")+COUNTIFS('S2'!$B$6:$B$23,$A106,'S2'!$E$6:$E$23,"Ambos")+COUNTIFS('S3'!$B$6:$B$19,$A106,'S3'!$E$6:$E$19,"Víctor")+COUNTIFS('S3'!$B$6:$B$19,$A106,'S3'!$E$6:$E$19,"Ambos")+COUNTIFS('S4'!$B$6:$B$20,$A106,'S4'!$E$6:$E$20,"Víctor")+COUNTIFS('S4'!$B$6:$B$20,$A106,'S4'!$E$6:$E$20,"Ambos")+COUNTIFS('S5'!$B$6:$B$20,$A106,'S5'!$E$6:$E$20,"Víctor")+COUNTIFS('S5'!$B$6:$B$20,$A106,'S5'!$E$6:$E$20,"Ambos")+COUNTIFS('S6'!$B$6:$B$17,$A106,'S6'!$E$6:$E$17,"Víctor")+COUNTIFS('S6'!$B$6:$B$17,$A106,'S6'!$E$6:$E$17,"Ambos")+COUNTIFS('S7'!$B$6:$B$19,$A106,'S7'!$E$6:$E$19,"Víctor")+COUNTIFS('S7'!$B$6:$B$19,$A106,'S7'!$E$6:$E$19,"Ambos")+COUNTIFS('S8'!$B$6:$B$23,$A106,'S8'!$E$6:$E$23,"Víctor")+COUNTIFS('S8'!$B$6:$B$23,$A106,'S8'!$E$6:$E$23,"Ambos")+COUNTIFS('S9'!$B$6:$B$15,$A106,'S9'!$E$6:$E$15,"Víctor")+COUNTIFS('S9'!$B$6:$B$15,$A106,'S9'!$E$6:$E$15,"Ambos")+COUNTIFS('S10'!$B$6:$B$13,$A106,'S10'!$E$6:$E$13,"Víctor")+COUNTIFS('S10'!$B$6:$B$13,$A106,'S10'!$E$6:$E$13,"Ambos")+COUNTIFS('Holgura'!$B$6:$B$11,$A106,'Holgura'!$E$6:$E$11,"Víctor")+COUNTIFS('Holgura'!$B$6:$B$11,$A106,'Holgura'!$E$6:$E$11,"Ambos")+COUNTIFS('Entrega'!$B$6:$B$9,$A106,'Entrega'!$E$6:$E$9,"Víctor")+COUNTIFS('Entrega'!$B$6:$B$9,$A106,'Entrega'!$E$6:$E$9,"Ambos")+COUNTIFS('Defensa'!$B$6:$B$10,$A106,'Defensa'!$E$6:$E$10,"Víctor")+COUNTIFS('Defensa'!$B$6:$B$10,$A106,'Defensa'!$E$6:$E$10,"Ambos")</f>
+        <f>COUNTIFS('S1'!$B$6:$B$32,$A106,'S1'!$E$6:$E$32,"Víctor")+COUNTIFS('S1'!$B$6:$B$32,$A106,'S1'!$E$6:$E$32,"Ambos")+COUNTIFS('S2'!$B$6:$B$23,$A106,'S2'!$E$6:$E$23,"Víctor")+COUNTIFS('S2'!$B$6:$B$23,$A106,'S2'!$E$6:$E$23,"Ambos")+COUNTIFS('S3'!$B$6:$B$24,$A106,'S3'!$E$6:$E$24,"Víctor")+COUNTIFS('S3'!$B$6:$B$24,$A106,'S3'!$E$6:$E$24,"Ambos")+COUNTIFS('S4'!$B$6:$B$22,$A106,'S4'!$E$6:$E$22,"Víctor")+COUNTIFS('S4'!$B$6:$B$22,$A106,'S4'!$E$6:$E$22,"Ambos")+COUNTIFS('S5'!$B$6:$B$20,$A106,'S5'!$E$6:$E$20,"Víctor")+COUNTIFS('S5'!$B$6:$B$20,$A106,'S5'!$E$6:$E$20,"Ambos")+COUNTIFS('S6'!$B$6:$B$17,$A106,'S6'!$E$6:$E$17,"Víctor")+COUNTIFS('S6'!$B$6:$B$17,$A106,'S6'!$E$6:$E$17,"Ambos")+COUNTIFS('S7'!$B$6:$B$19,$A106,'S7'!$E$6:$E$19,"Víctor")+COUNTIFS('S7'!$B$6:$B$19,$A106,'S7'!$E$6:$E$19,"Ambos")+COUNTIFS('S8'!$B$6:$B$23,$A106,'S8'!$E$6:$E$23,"Víctor")+COUNTIFS('S8'!$B$6:$B$23,$A106,'S8'!$E$6:$E$23,"Ambos")+COUNTIFS('S9'!$B$6:$B$15,$A106,'S9'!$E$6:$E$15,"Víctor")+COUNTIFS('S9'!$B$6:$B$15,$A106,'S9'!$E$6:$E$15,"Ambos")+COUNTIFS('S10'!$B$6:$B$13,$A106,'S10'!$E$6:$E$13,"Víctor")+COUNTIFS('S10'!$B$6:$B$13,$A106,'S10'!$E$6:$E$13,"Ambos")+COUNTIFS('Holgura'!$B$6:$B$11,$A106,'Holgura'!$E$6:$E$11,"Víctor")+COUNTIFS('Holgura'!$B$6:$B$11,$A106,'Holgura'!$E$6:$E$11,"Ambos")+COUNTIFS('Entrega'!$B$6:$B$9,$A106,'Entrega'!$E$6:$E$9,"Víctor")+COUNTIFS('Entrega'!$B$6:$B$9,$A106,'Entrega'!$E$6:$E$9,"Ambos")+COUNTIFS('Defensa'!$B$6:$B$10,$A106,'Defensa'!$E$6:$E$10,"Víctor")+COUNTIFS('Defensa'!$B$6:$B$10,$A106,'Defensa'!$E$6:$E$10,"Ambos")</f>
         <v/>
       </c>
       <c r="G106" s="21">
-        <f>COUNTIFS('S1'!$B$6:$B$32,$A106,'S1'!$E$6:$E$32,"Diego")+COUNTIFS('S1'!$B$6:$B$32,$A106,'S1'!$E$6:$E$32,"Ambos")+COUNTIFS('S2'!$B$6:$B$23,$A106,'S2'!$E$6:$E$23,"Diego")+COUNTIFS('S2'!$B$6:$B$23,$A106,'S2'!$E$6:$E$23,"Ambos")+COUNTIFS('S3'!$B$6:$B$19,$A106,'S3'!$E$6:$E$19,"Diego")+COUNTIFS('S3'!$B$6:$B$19,$A106,'S3'!$E$6:$E$19,"Ambos")+COUNTIFS('S4'!$B$6:$B$20,$A106,'S4'!$E$6:$E$20,"Diego")+COUNTIFS('S4'!$B$6:$B$20,$A106,'S4'!$E$6:$E$20,"Ambos")+COUNTIFS('S5'!$B$6:$B$20,$A106,'S5'!$E$6:$E$20,"Diego")+COUNTIFS('S5'!$B$6:$B$20,$A106,'S5'!$E$6:$E$20,"Ambos")+COUNTIFS('S6'!$B$6:$B$17,$A106,'S6'!$E$6:$E$17,"Diego")+COUNTIFS('S6'!$B$6:$B$17,$A106,'S6'!$E$6:$E$17,"Ambos")+COUNTIFS('S7'!$B$6:$B$19,$A106,'S7'!$E$6:$E$19,"Diego")+COUNTIFS('S7'!$B$6:$B$19,$A106,'S7'!$E$6:$E$19,"Ambos")+COUNTIFS('S8'!$B$6:$B$23,$A106,'S8'!$E$6:$E$23,"Diego")+COUNTIFS('S8'!$B$6:$B$23,$A106,'S8'!$E$6:$E$23,"Ambos")+COUNTIFS('S9'!$B$6:$B$15,$A106,'S9'!$E$6:$E$15,"Diego")+COUNTIFS('S9'!$B$6:$B$15,$A106,'S9'!$E$6:$E$15,"Ambos")+COUNTIFS('S10'!$B$6:$B$13,$A106,'S10'!$E$6:$E$13,"Diego")+COUNTIFS('S10'!$B$6:$B$13,$A106,'S10'!$E$6:$E$13,"Ambos")+COUNTIFS('Holgura'!$B$6:$B$11,$A106,'Holgura'!$E$6:$E$11,"Diego")+COUNTIFS('Holgura'!$B$6:$B$11,$A106,'Holgura'!$E$6:$E$11,"Ambos")+COUNTIFS('Entrega'!$B$6:$B$9,$A106,'Entrega'!$E$6:$E$9,"Diego")+COUNTIFS('Entrega'!$B$6:$B$9,$A106,'Entrega'!$E$6:$E$9,"Ambos")+COUNTIFS('Defensa'!$B$6:$B$10,$A106,'Defensa'!$E$6:$E$10,"Diego")+COUNTIFS('Defensa'!$B$6:$B$10,$A106,'Defensa'!$E$6:$E$10,"Ambos")</f>
+        <f>COUNTIFS('S1'!$B$6:$B$32,$A106,'S1'!$E$6:$E$32,"Diego")+COUNTIFS('S1'!$B$6:$B$32,$A106,'S1'!$E$6:$E$32,"Ambos")+COUNTIFS('S2'!$B$6:$B$23,$A106,'S2'!$E$6:$E$23,"Diego")+COUNTIFS('S2'!$B$6:$B$23,$A106,'S2'!$E$6:$E$23,"Ambos")+COUNTIFS('S3'!$B$6:$B$24,$A106,'S3'!$E$6:$E$24,"Diego")+COUNTIFS('S3'!$B$6:$B$24,$A106,'S3'!$E$6:$E$24,"Ambos")+COUNTIFS('S4'!$B$6:$B$22,$A106,'S4'!$E$6:$E$22,"Diego")+COUNTIFS('S4'!$B$6:$B$22,$A106,'S4'!$E$6:$E$22,"Ambos")+COUNTIFS('S5'!$B$6:$B$20,$A106,'S5'!$E$6:$E$20,"Diego")+COUNTIFS('S5'!$B$6:$B$20,$A106,'S5'!$E$6:$E$20,"Ambos")+COUNTIFS('S6'!$B$6:$B$17,$A106,'S6'!$E$6:$E$17,"Diego")+COUNTIFS('S6'!$B$6:$B$17,$A106,'S6'!$E$6:$E$17,"Ambos")+COUNTIFS('S7'!$B$6:$B$19,$A106,'S7'!$E$6:$E$19,"Diego")+COUNTIFS('S7'!$B$6:$B$19,$A106,'S7'!$E$6:$E$19,"Ambos")+COUNTIFS('S8'!$B$6:$B$23,$A106,'S8'!$E$6:$E$23,"Diego")+COUNTIFS('S8'!$B$6:$B$23,$A106,'S8'!$E$6:$E$23,"Ambos")+COUNTIFS('S9'!$B$6:$B$15,$A106,'S9'!$E$6:$E$15,"Diego")+COUNTIFS('S9'!$B$6:$B$15,$A106,'S9'!$E$6:$E$15,"Ambos")+COUNTIFS('S10'!$B$6:$B$13,$A106,'S10'!$E$6:$E$13,"Diego")+COUNTIFS('S10'!$B$6:$B$13,$A106,'S10'!$E$6:$E$13,"Ambos")+COUNTIFS('Holgura'!$B$6:$B$11,$A106,'Holgura'!$E$6:$E$11,"Diego")+COUNTIFS('Holgura'!$B$6:$B$11,$A106,'Holgura'!$E$6:$E$11,"Ambos")+COUNTIFS('Entrega'!$B$6:$B$9,$A106,'Entrega'!$E$6:$E$9,"Diego")+COUNTIFS('Entrega'!$B$6:$B$9,$A106,'Entrega'!$E$6:$E$9,"Ambos")+COUNTIFS('Defensa'!$B$6:$B$10,$A106,'Defensa'!$E$6:$E$10,"Diego")+COUNTIFS('Defensa'!$B$6:$B$10,$A106,'Defensa'!$E$6:$E$10,"Ambos")</f>
         <v/>
       </c>
     </row>
@@ -11638,19 +11659,19 @@
         <v/>
       </c>
       <c r="D107" s="21">
-        <f>SUMIFS('S1'!$I$6:$I$32,'S1'!$B$6:$B$32,$A107,'S1'!$E$6:$E$32,"Víctor")+SUMIFS('S1'!$I$6:$I$32,'S1'!$B$6:$B$32,$A107,'S1'!$E$6:$E$32,"Ambos")+SUMIFS('S2'!$I$6:$I$23,'S2'!$B$6:$B$23,$A107,'S2'!$E$6:$E$23,"Víctor")+SUMIFS('S2'!$I$6:$I$23,'S2'!$B$6:$B$23,$A107,'S2'!$E$6:$E$23,"Ambos")+SUMIFS('S3'!$I$6:$I$19,'S3'!$B$6:$B$19,$A107,'S3'!$E$6:$E$19,"Víctor")+SUMIFS('S3'!$I$6:$I$19,'S3'!$B$6:$B$19,$A107,'S3'!$E$6:$E$19,"Ambos")+SUMIFS('S4'!$I$6:$I$20,'S4'!$B$6:$B$20,$A107,'S4'!$E$6:$E$20,"Víctor")+SUMIFS('S4'!$I$6:$I$20,'S4'!$B$6:$B$20,$A107,'S4'!$E$6:$E$20,"Ambos")+SUMIFS('S5'!$I$6:$I$20,'S5'!$B$6:$B$20,$A107,'S5'!$E$6:$E$20,"Víctor")+SUMIFS('S5'!$I$6:$I$20,'S5'!$B$6:$B$20,$A107,'S5'!$E$6:$E$20,"Ambos")+SUMIFS('S6'!$I$6:$I$17,'S6'!$B$6:$B$17,$A107,'S6'!$E$6:$E$17,"Víctor")+SUMIFS('S6'!$I$6:$I$17,'S6'!$B$6:$B$17,$A107,'S6'!$E$6:$E$17,"Ambos")+SUMIFS('S7'!$I$6:$I$19,'S7'!$B$6:$B$19,$A107,'S7'!$E$6:$E$19,"Víctor")+SUMIFS('S7'!$I$6:$I$19,'S7'!$B$6:$B$19,$A107,'S7'!$E$6:$E$19,"Ambos")+SUMIFS('S8'!$I$6:$I$23,'S8'!$B$6:$B$23,$A107,'S8'!$E$6:$E$23,"Víctor")+SUMIFS('S8'!$I$6:$I$23,'S8'!$B$6:$B$23,$A107,'S8'!$E$6:$E$23,"Ambos")+SUMIFS('S9'!$I$6:$I$15,'S9'!$B$6:$B$15,$A107,'S9'!$E$6:$E$15,"Víctor")+SUMIFS('S9'!$I$6:$I$15,'S9'!$B$6:$B$15,$A107,'S9'!$E$6:$E$15,"Ambos")+SUMIFS('S10'!$I$6:$I$13,'S10'!$B$6:$B$13,$A107,'S10'!$E$6:$E$13,"Víctor")+SUMIFS('S10'!$I$6:$I$13,'S10'!$B$6:$B$13,$A107,'S10'!$E$6:$E$13,"Ambos")+SUMIFS('Holgura'!$I$6:$I$11,'Holgura'!$B$6:$B$11,$A107,'Holgura'!$E$6:$E$11,"Víctor")+SUMIFS('Holgura'!$I$6:$I$11,'Holgura'!$B$6:$B$11,$A107,'Holgura'!$E$6:$E$11,"Ambos")+SUMIFS('Entrega'!$I$6:$I$9,'Entrega'!$B$6:$B$9,$A107,'Entrega'!$E$6:$E$9,"Víctor")+SUMIFS('Entrega'!$I$6:$I$9,'Entrega'!$B$6:$B$9,$A107,'Entrega'!$E$6:$E$9,"Ambos")+SUMIFS('Defensa'!$I$6:$I$10,'Defensa'!$B$6:$B$10,$A107,'Defensa'!$E$6:$E$10,"Víctor")+SUMIFS('Defensa'!$I$6:$I$10,'Defensa'!$B$6:$B$10,$A107,'Defensa'!$E$6:$E$10,"Ambos")</f>
+        <f>SUMIFS('S1'!$I$6:$I$32,'S1'!$B$6:$B$32,$A107,'S1'!$E$6:$E$32,"Víctor")+SUMIFS('S1'!$I$6:$I$32,'S1'!$B$6:$B$32,$A107,'S1'!$E$6:$E$32,"Ambos")+SUMIFS('S2'!$I$6:$I$23,'S2'!$B$6:$B$23,$A107,'S2'!$E$6:$E$23,"Víctor")+SUMIFS('S2'!$I$6:$I$23,'S2'!$B$6:$B$23,$A107,'S2'!$E$6:$E$23,"Ambos")+SUMIFS('S3'!$I$6:$I$24,'S3'!$B$6:$B$24,$A107,'S3'!$E$6:$E$24,"Víctor")+SUMIFS('S3'!$I$6:$I$24,'S3'!$B$6:$B$24,$A107,'S3'!$E$6:$E$24,"Ambos")+SUMIFS('S4'!$I$6:$I$22,'S4'!$B$6:$B$22,$A107,'S4'!$E$6:$E$22,"Víctor")+SUMIFS('S4'!$I$6:$I$22,'S4'!$B$6:$B$22,$A107,'S4'!$E$6:$E$22,"Ambos")+SUMIFS('S5'!$I$6:$I$20,'S5'!$B$6:$B$20,$A107,'S5'!$E$6:$E$20,"Víctor")+SUMIFS('S5'!$I$6:$I$20,'S5'!$B$6:$B$20,$A107,'S5'!$E$6:$E$20,"Ambos")+SUMIFS('S6'!$I$6:$I$17,'S6'!$B$6:$B$17,$A107,'S6'!$E$6:$E$17,"Víctor")+SUMIFS('S6'!$I$6:$I$17,'S6'!$B$6:$B$17,$A107,'S6'!$E$6:$E$17,"Ambos")+SUMIFS('S7'!$I$6:$I$19,'S7'!$B$6:$B$19,$A107,'S7'!$E$6:$E$19,"Víctor")+SUMIFS('S7'!$I$6:$I$19,'S7'!$B$6:$B$19,$A107,'S7'!$E$6:$E$19,"Ambos")+SUMIFS('S8'!$I$6:$I$23,'S8'!$B$6:$B$23,$A107,'S8'!$E$6:$E$23,"Víctor")+SUMIFS('S8'!$I$6:$I$23,'S8'!$B$6:$B$23,$A107,'S8'!$E$6:$E$23,"Ambos")+SUMIFS('S9'!$I$6:$I$15,'S9'!$B$6:$B$15,$A107,'S9'!$E$6:$E$15,"Víctor")+SUMIFS('S9'!$I$6:$I$15,'S9'!$B$6:$B$15,$A107,'S9'!$E$6:$E$15,"Ambos")+SUMIFS('S10'!$I$6:$I$13,'S10'!$B$6:$B$13,$A107,'S10'!$E$6:$E$13,"Víctor")+SUMIFS('S10'!$I$6:$I$13,'S10'!$B$6:$B$13,$A107,'S10'!$E$6:$E$13,"Ambos")+SUMIFS('Holgura'!$I$6:$I$11,'Holgura'!$B$6:$B$11,$A107,'Holgura'!$E$6:$E$11,"Víctor")+SUMIFS('Holgura'!$I$6:$I$11,'Holgura'!$B$6:$B$11,$A107,'Holgura'!$E$6:$E$11,"Ambos")+SUMIFS('Entrega'!$I$6:$I$9,'Entrega'!$B$6:$B$9,$A107,'Entrega'!$E$6:$E$9,"Víctor")+SUMIFS('Entrega'!$I$6:$I$9,'Entrega'!$B$6:$B$9,$A107,'Entrega'!$E$6:$E$9,"Ambos")+SUMIFS('Defensa'!$I$6:$I$10,'Defensa'!$B$6:$B$10,$A107,'Defensa'!$E$6:$E$10,"Víctor")+SUMIFS('Defensa'!$I$6:$I$10,'Defensa'!$B$6:$B$10,$A107,'Defensa'!$E$6:$E$10,"Ambos")</f>
         <v/>
       </c>
       <c r="E107" s="21">
-        <f>SUMIFS('S1'!$I$6:$I$32,'S1'!$B$6:$B$32,$A107,'S1'!$E$6:$E$32,"Diego")+SUMIFS('S1'!$I$6:$I$32,'S1'!$B$6:$B$32,$A107,'S1'!$E$6:$E$32,"Ambos")+SUMIFS('S2'!$I$6:$I$23,'S2'!$B$6:$B$23,$A107,'S2'!$E$6:$E$23,"Diego")+SUMIFS('S2'!$I$6:$I$23,'S2'!$B$6:$B$23,$A107,'S2'!$E$6:$E$23,"Ambos")+SUMIFS('S3'!$I$6:$I$19,'S3'!$B$6:$B$19,$A107,'S3'!$E$6:$E$19,"Diego")+SUMIFS('S3'!$I$6:$I$19,'S3'!$B$6:$B$19,$A107,'S3'!$E$6:$E$19,"Ambos")+SUMIFS('S4'!$I$6:$I$20,'S4'!$B$6:$B$20,$A107,'S4'!$E$6:$E$20,"Diego")+SUMIFS('S4'!$I$6:$I$20,'S4'!$B$6:$B$20,$A107,'S4'!$E$6:$E$20,"Ambos")+SUMIFS('S5'!$I$6:$I$20,'S5'!$B$6:$B$20,$A107,'S5'!$E$6:$E$20,"Diego")+SUMIFS('S5'!$I$6:$I$20,'S5'!$B$6:$B$20,$A107,'S5'!$E$6:$E$20,"Ambos")+SUMIFS('S6'!$I$6:$I$17,'S6'!$B$6:$B$17,$A107,'S6'!$E$6:$E$17,"Diego")+SUMIFS('S6'!$I$6:$I$17,'S6'!$B$6:$B$17,$A107,'S6'!$E$6:$E$17,"Ambos")+SUMIFS('S7'!$I$6:$I$19,'S7'!$B$6:$B$19,$A107,'S7'!$E$6:$E$19,"Diego")+SUMIFS('S7'!$I$6:$I$19,'S7'!$B$6:$B$19,$A107,'S7'!$E$6:$E$19,"Ambos")+SUMIFS('S8'!$I$6:$I$23,'S8'!$B$6:$B$23,$A107,'S8'!$E$6:$E$23,"Diego")+SUMIFS('S8'!$I$6:$I$23,'S8'!$B$6:$B$23,$A107,'S8'!$E$6:$E$23,"Ambos")+SUMIFS('S9'!$I$6:$I$15,'S9'!$B$6:$B$15,$A107,'S9'!$E$6:$E$15,"Diego")+SUMIFS('S9'!$I$6:$I$15,'S9'!$B$6:$B$15,$A107,'S9'!$E$6:$E$15,"Ambos")+SUMIFS('S10'!$I$6:$I$13,'S10'!$B$6:$B$13,$A107,'S10'!$E$6:$E$13,"Diego")+SUMIFS('S10'!$I$6:$I$13,'S10'!$B$6:$B$13,$A107,'S10'!$E$6:$E$13,"Ambos")+SUMIFS('Holgura'!$I$6:$I$11,'Holgura'!$B$6:$B$11,$A107,'Holgura'!$E$6:$E$11,"Diego")+SUMIFS('Holgura'!$I$6:$I$11,'Holgura'!$B$6:$B$11,$A107,'Holgura'!$E$6:$E$11,"Ambos")+SUMIFS('Entrega'!$I$6:$I$9,'Entrega'!$B$6:$B$9,$A107,'Entrega'!$E$6:$E$9,"Diego")+SUMIFS('Entrega'!$I$6:$I$9,'Entrega'!$B$6:$B$9,$A107,'Entrega'!$E$6:$E$9,"Ambos")+SUMIFS('Defensa'!$I$6:$I$10,'Defensa'!$B$6:$B$10,$A107,'Defensa'!$E$6:$E$10,"Diego")+SUMIFS('Defensa'!$I$6:$I$10,'Defensa'!$B$6:$B$10,$A107,'Defensa'!$E$6:$E$10,"Ambos")</f>
+        <f>SUMIFS('S1'!$I$6:$I$32,'S1'!$B$6:$B$32,$A107,'S1'!$E$6:$E$32,"Diego")+SUMIFS('S1'!$I$6:$I$32,'S1'!$B$6:$B$32,$A107,'S1'!$E$6:$E$32,"Ambos")+SUMIFS('S2'!$I$6:$I$23,'S2'!$B$6:$B$23,$A107,'S2'!$E$6:$E$23,"Diego")+SUMIFS('S2'!$I$6:$I$23,'S2'!$B$6:$B$23,$A107,'S2'!$E$6:$E$23,"Ambos")+SUMIFS('S3'!$I$6:$I$24,'S3'!$B$6:$B$24,$A107,'S3'!$E$6:$E$24,"Diego")+SUMIFS('S3'!$I$6:$I$24,'S3'!$B$6:$B$24,$A107,'S3'!$E$6:$E$24,"Ambos")+SUMIFS('S4'!$I$6:$I$22,'S4'!$B$6:$B$22,$A107,'S4'!$E$6:$E$22,"Diego")+SUMIFS('S4'!$I$6:$I$22,'S4'!$B$6:$B$22,$A107,'S4'!$E$6:$E$22,"Ambos")+SUMIFS('S5'!$I$6:$I$20,'S5'!$B$6:$B$20,$A107,'S5'!$E$6:$E$20,"Diego")+SUMIFS('S5'!$I$6:$I$20,'S5'!$B$6:$B$20,$A107,'S5'!$E$6:$E$20,"Ambos")+SUMIFS('S6'!$I$6:$I$17,'S6'!$B$6:$B$17,$A107,'S6'!$E$6:$E$17,"Diego")+SUMIFS('S6'!$I$6:$I$17,'S6'!$B$6:$B$17,$A107,'S6'!$E$6:$E$17,"Ambos")+SUMIFS('S7'!$I$6:$I$19,'S7'!$B$6:$B$19,$A107,'S7'!$E$6:$E$19,"Diego")+SUMIFS('S7'!$I$6:$I$19,'S7'!$B$6:$B$19,$A107,'S7'!$E$6:$E$19,"Ambos")+SUMIFS('S8'!$I$6:$I$23,'S8'!$B$6:$B$23,$A107,'S8'!$E$6:$E$23,"Diego")+SUMIFS('S8'!$I$6:$I$23,'S8'!$B$6:$B$23,$A107,'S8'!$E$6:$E$23,"Ambos")+SUMIFS('S9'!$I$6:$I$15,'S9'!$B$6:$B$15,$A107,'S9'!$E$6:$E$15,"Diego")+SUMIFS('S9'!$I$6:$I$15,'S9'!$B$6:$B$15,$A107,'S9'!$E$6:$E$15,"Ambos")+SUMIFS('S10'!$I$6:$I$13,'S10'!$B$6:$B$13,$A107,'S10'!$E$6:$E$13,"Diego")+SUMIFS('S10'!$I$6:$I$13,'S10'!$B$6:$B$13,$A107,'S10'!$E$6:$E$13,"Ambos")+SUMIFS('Holgura'!$I$6:$I$11,'Holgura'!$B$6:$B$11,$A107,'Holgura'!$E$6:$E$11,"Diego")+SUMIFS('Holgura'!$I$6:$I$11,'Holgura'!$B$6:$B$11,$A107,'Holgura'!$E$6:$E$11,"Ambos")+SUMIFS('Entrega'!$I$6:$I$9,'Entrega'!$B$6:$B$9,$A107,'Entrega'!$E$6:$E$9,"Diego")+SUMIFS('Entrega'!$I$6:$I$9,'Entrega'!$B$6:$B$9,$A107,'Entrega'!$E$6:$E$9,"Ambos")+SUMIFS('Defensa'!$I$6:$I$10,'Defensa'!$B$6:$B$10,$A107,'Defensa'!$E$6:$E$10,"Diego")+SUMIFS('Defensa'!$I$6:$I$10,'Defensa'!$B$6:$B$10,$A107,'Defensa'!$E$6:$E$10,"Ambos")</f>
         <v/>
       </c>
       <c r="F107" s="21">
-        <f>COUNTIFS('S1'!$B$6:$B$32,$A107,'S1'!$E$6:$E$32,"Víctor")+COUNTIFS('S1'!$B$6:$B$32,$A107,'S1'!$E$6:$E$32,"Ambos")+COUNTIFS('S2'!$B$6:$B$23,$A107,'S2'!$E$6:$E$23,"Víctor")+COUNTIFS('S2'!$B$6:$B$23,$A107,'S2'!$E$6:$E$23,"Ambos")+COUNTIFS('S3'!$B$6:$B$19,$A107,'S3'!$E$6:$E$19,"Víctor")+COUNTIFS('S3'!$B$6:$B$19,$A107,'S3'!$E$6:$E$19,"Ambos")+COUNTIFS('S4'!$B$6:$B$20,$A107,'S4'!$E$6:$E$20,"Víctor")+COUNTIFS('S4'!$B$6:$B$20,$A107,'S4'!$E$6:$E$20,"Ambos")+COUNTIFS('S5'!$B$6:$B$20,$A107,'S5'!$E$6:$E$20,"Víctor")+COUNTIFS('S5'!$B$6:$B$20,$A107,'S5'!$E$6:$E$20,"Ambos")+COUNTIFS('S6'!$B$6:$B$17,$A107,'S6'!$E$6:$E$17,"Víctor")+COUNTIFS('S6'!$B$6:$B$17,$A107,'S6'!$E$6:$E$17,"Ambos")+COUNTIFS('S7'!$B$6:$B$19,$A107,'S7'!$E$6:$E$19,"Víctor")+COUNTIFS('S7'!$B$6:$B$19,$A107,'S7'!$E$6:$E$19,"Ambos")+COUNTIFS('S8'!$B$6:$B$23,$A107,'S8'!$E$6:$E$23,"Víctor")+COUNTIFS('S8'!$B$6:$B$23,$A107,'S8'!$E$6:$E$23,"Ambos")+COUNTIFS('S9'!$B$6:$B$15,$A107,'S9'!$E$6:$E$15,"Víctor")+COUNTIFS('S9'!$B$6:$B$15,$A107,'S9'!$E$6:$E$15,"Ambos")+COUNTIFS('S10'!$B$6:$B$13,$A107,'S10'!$E$6:$E$13,"Víctor")+COUNTIFS('S10'!$B$6:$B$13,$A107,'S10'!$E$6:$E$13,"Ambos")+COUNTIFS('Holgura'!$B$6:$B$11,$A107,'Holgura'!$E$6:$E$11,"Víctor")+COUNTIFS('Holgura'!$B$6:$B$11,$A107,'Holgura'!$E$6:$E$11,"Ambos")+COUNTIFS('Entrega'!$B$6:$B$9,$A107,'Entrega'!$E$6:$E$9,"Víctor")+COUNTIFS('Entrega'!$B$6:$B$9,$A107,'Entrega'!$E$6:$E$9,"Ambos")+COUNTIFS('Defensa'!$B$6:$B$10,$A107,'Defensa'!$E$6:$E$10,"Víctor")+COUNTIFS('Defensa'!$B$6:$B$10,$A107,'Defensa'!$E$6:$E$10,"Ambos")</f>
+        <f>COUNTIFS('S1'!$B$6:$B$32,$A107,'S1'!$E$6:$E$32,"Víctor")+COUNTIFS('S1'!$B$6:$B$32,$A107,'S1'!$E$6:$E$32,"Ambos")+COUNTIFS('S2'!$B$6:$B$23,$A107,'S2'!$E$6:$E$23,"Víctor")+COUNTIFS('S2'!$B$6:$B$23,$A107,'S2'!$E$6:$E$23,"Ambos")+COUNTIFS('S3'!$B$6:$B$24,$A107,'S3'!$E$6:$E$24,"Víctor")+COUNTIFS('S3'!$B$6:$B$24,$A107,'S3'!$E$6:$E$24,"Ambos")+COUNTIFS('S4'!$B$6:$B$22,$A107,'S4'!$E$6:$E$22,"Víctor")+COUNTIFS('S4'!$B$6:$B$22,$A107,'S4'!$E$6:$E$22,"Ambos")+COUNTIFS('S5'!$B$6:$B$20,$A107,'S5'!$E$6:$E$20,"Víctor")+COUNTIFS('S5'!$B$6:$B$20,$A107,'S5'!$E$6:$E$20,"Ambos")+COUNTIFS('S6'!$B$6:$B$17,$A107,'S6'!$E$6:$E$17,"Víctor")+COUNTIFS('S6'!$B$6:$B$17,$A107,'S6'!$E$6:$E$17,"Ambos")+COUNTIFS('S7'!$B$6:$B$19,$A107,'S7'!$E$6:$E$19,"Víctor")+COUNTIFS('S7'!$B$6:$B$19,$A107,'S7'!$E$6:$E$19,"Ambos")+COUNTIFS('S8'!$B$6:$B$23,$A107,'S8'!$E$6:$E$23,"Víctor")+COUNTIFS('S8'!$B$6:$B$23,$A107,'S8'!$E$6:$E$23,"Ambos")+COUNTIFS('S9'!$B$6:$B$15,$A107,'S9'!$E$6:$E$15,"Víctor")+COUNTIFS('S9'!$B$6:$B$15,$A107,'S9'!$E$6:$E$15,"Ambos")+COUNTIFS('S10'!$B$6:$B$13,$A107,'S10'!$E$6:$E$13,"Víctor")+COUNTIFS('S10'!$B$6:$B$13,$A107,'S10'!$E$6:$E$13,"Ambos")+COUNTIFS('Holgura'!$B$6:$B$11,$A107,'Holgura'!$E$6:$E$11,"Víctor")+COUNTIFS('Holgura'!$B$6:$B$11,$A107,'Holgura'!$E$6:$E$11,"Ambos")+COUNTIFS('Entrega'!$B$6:$B$9,$A107,'Entrega'!$E$6:$E$9,"Víctor")+COUNTIFS('Entrega'!$B$6:$B$9,$A107,'Entrega'!$E$6:$E$9,"Ambos")+COUNTIFS('Defensa'!$B$6:$B$10,$A107,'Defensa'!$E$6:$E$10,"Víctor")+COUNTIFS('Defensa'!$B$6:$B$10,$A107,'Defensa'!$E$6:$E$10,"Ambos")</f>
         <v/>
       </c>
       <c r="G107" s="21">
-        <f>COUNTIFS('S1'!$B$6:$B$32,$A107,'S1'!$E$6:$E$32,"Diego")+COUNTIFS('S1'!$B$6:$B$32,$A107,'S1'!$E$6:$E$32,"Ambos")+COUNTIFS('S2'!$B$6:$B$23,$A107,'S2'!$E$6:$E$23,"Diego")+COUNTIFS('S2'!$B$6:$B$23,$A107,'S2'!$E$6:$E$23,"Ambos")+COUNTIFS('S3'!$B$6:$B$19,$A107,'S3'!$E$6:$E$19,"Diego")+COUNTIFS('S3'!$B$6:$B$19,$A107,'S3'!$E$6:$E$19,"Ambos")+COUNTIFS('S4'!$B$6:$B$20,$A107,'S4'!$E$6:$E$20,"Diego")+COUNTIFS('S4'!$B$6:$B$20,$A107,'S4'!$E$6:$E$20,"Ambos")+COUNTIFS('S5'!$B$6:$B$20,$A107,'S5'!$E$6:$E$20,"Diego")+COUNTIFS('S5'!$B$6:$B$20,$A107,'S5'!$E$6:$E$20,"Ambos")+COUNTIFS('S6'!$B$6:$B$17,$A107,'S6'!$E$6:$E$17,"Diego")+COUNTIFS('S6'!$B$6:$B$17,$A107,'S6'!$E$6:$E$17,"Ambos")+COUNTIFS('S7'!$B$6:$B$19,$A107,'S7'!$E$6:$E$19,"Diego")+COUNTIFS('S7'!$B$6:$B$19,$A107,'S7'!$E$6:$E$19,"Ambos")+COUNTIFS('S8'!$B$6:$B$23,$A107,'S8'!$E$6:$E$23,"Diego")+COUNTIFS('S8'!$B$6:$B$23,$A107,'S8'!$E$6:$E$23,"Ambos")+COUNTIFS('S9'!$B$6:$B$15,$A107,'S9'!$E$6:$E$15,"Diego")+COUNTIFS('S9'!$B$6:$B$15,$A107,'S9'!$E$6:$E$15,"Ambos")+COUNTIFS('S10'!$B$6:$B$13,$A107,'S10'!$E$6:$E$13,"Diego")+COUNTIFS('S10'!$B$6:$B$13,$A107,'S10'!$E$6:$E$13,"Ambos")+COUNTIFS('Holgura'!$B$6:$B$11,$A107,'Holgura'!$E$6:$E$11,"Diego")+COUNTIFS('Holgura'!$B$6:$B$11,$A107,'Holgura'!$E$6:$E$11,"Ambos")+COUNTIFS('Entrega'!$B$6:$B$9,$A107,'Entrega'!$E$6:$E$9,"Diego")+COUNTIFS('Entrega'!$B$6:$B$9,$A107,'Entrega'!$E$6:$E$9,"Ambos")+COUNTIFS('Defensa'!$B$6:$B$10,$A107,'Defensa'!$E$6:$E$10,"Diego")+COUNTIFS('Defensa'!$B$6:$B$10,$A107,'Defensa'!$E$6:$E$10,"Ambos")</f>
+        <f>COUNTIFS('S1'!$B$6:$B$32,$A107,'S1'!$E$6:$E$32,"Diego")+COUNTIFS('S1'!$B$6:$B$32,$A107,'S1'!$E$6:$E$32,"Ambos")+COUNTIFS('S2'!$B$6:$B$23,$A107,'S2'!$E$6:$E$23,"Diego")+COUNTIFS('S2'!$B$6:$B$23,$A107,'S2'!$E$6:$E$23,"Ambos")+COUNTIFS('S3'!$B$6:$B$24,$A107,'S3'!$E$6:$E$24,"Diego")+COUNTIFS('S3'!$B$6:$B$24,$A107,'S3'!$E$6:$E$24,"Ambos")+COUNTIFS('S4'!$B$6:$B$22,$A107,'S4'!$E$6:$E$22,"Diego")+COUNTIFS('S4'!$B$6:$B$22,$A107,'S4'!$E$6:$E$22,"Ambos")+COUNTIFS('S5'!$B$6:$B$20,$A107,'S5'!$E$6:$E$20,"Diego")+COUNTIFS('S5'!$B$6:$B$20,$A107,'S5'!$E$6:$E$20,"Ambos")+COUNTIFS('S6'!$B$6:$B$17,$A107,'S6'!$E$6:$E$17,"Diego")+COUNTIFS('S6'!$B$6:$B$17,$A107,'S6'!$E$6:$E$17,"Ambos")+COUNTIFS('S7'!$B$6:$B$19,$A107,'S7'!$E$6:$E$19,"Diego")+COUNTIFS('S7'!$B$6:$B$19,$A107,'S7'!$E$6:$E$19,"Ambos")+COUNTIFS('S8'!$B$6:$B$23,$A107,'S8'!$E$6:$E$23,"Diego")+COUNTIFS('S8'!$B$6:$B$23,$A107,'S8'!$E$6:$E$23,"Ambos")+COUNTIFS('S9'!$B$6:$B$15,$A107,'S9'!$E$6:$E$15,"Diego")+COUNTIFS('S9'!$B$6:$B$15,$A107,'S9'!$E$6:$E$15,"Ambos")+COUNTIFS('S10'!$B$6:$B$13,$A107,'S10'!$E$6:$E$13,"Diego")+COUNTIFS('S10'!$B$6:$B$13,$A107,'S10'!$E$6:$E$13,"Ambos")+COUNTIFS('Holgura'!$B$6:$B$11,$A107,'Holgura'!$E$6:$E$11,"Diego")+COUNTIFS('Holgura'!$B$6:$B$11,$A107,'Holgura'!$E$6:$E$11,"Ambos")+COUNTIFS('Entrega'!$B$6:$B$9,$A107,'Entrega'!$E$6:$E$9,"Diego")+COUNTIFS('Entrega'!$B$6:$B$9,$A107,'Entrega'!$E$6:$E$9,"Ambos")+COUNTIFS('Defensa'!$B$6:$B$10,$A107,'Defensa'!$E$6:$E$10,"Diego")+COUNTIFS('Defensa'!$B$6:$B$10,$A107,'Defensa'!$E$6:$E$10,"Ambos")</f>
         <v/>
       </c>
     </row>
@@ -11667,19 +11688,19 @@
         <v/>
       </c>
       <c r="D108" s="21">
-        <f>SUMIFS('S1'!$I$6:$I$32,'S1'!$B$6:$B$32,$A108,'S1'!$E$6:$E$32,"Víctor")+SUMIFS('S1'!$I$6:$I$32,'S1'!$B$6:$B$32,$A108,'S1'!$E$6:$E$32,"Ambos")+SUMIFS('S2'!$I$6:$I$23,'S2'!$B$6:$B$23,$A108,'S2'!$E$6:$E$23,"Víctor")+SUMIFS('S2'!$I$6:$I$23,'S2'!$B$6:$B$23,$A108,'S2'!$E$6:$E$23,"Ambos")+SUMIFS('S3'!$I$6:$I$19,'S3'!$B$6:$B$19,$A108,'S3'!$E$6:$E$19,"Víctor")+SUMIFS('S3'!$I$6:$I$19,'S3'!$B$6:$B$19,$A108,'S3'!$E$6:$E$19,"Ambos")+SUMIFS('S4'!$I$6:$I$20,'S4'!$B$6:$B$20,$A108,'S4'!$E$6:$E$20,"Víctor")+SUMIFS('S4'!$I$6:$I$20,'S4'!$B$6:$B$20,$A108,'S4'!$E$6:$E$20,"Ambos")+SUMIFS('S5'!$I$6:$I$20,'S5'!$B$6:$B$20,$A108,'S5'!$E$6:$E$20,"Víctor")+SUMIFS('S5'!$I$6:$I$20,'S5'!$B$6:$B$20,$A108,'S5'!$E$6:$E$20,"Ambos")+SUMIFS('S6'!$I$6:$I$17,'S6'!$B$6:$B$17,$A108,'S6'!$E$6:$E$17,"Víctor")+SUMIFS('S6'!$I$6:$I$17,'S6'!$B$6:$B$17,$A108,'S6'!$E$6:$E$17,"Ambos")+SUMIFS('S7'!$I$6:$I$19,'S7'!$B$6:$B$19,$A108,'S7'!$E$6:$E$19,"Víctor")+SUMIFS('S7'!$I$6:$I$19,'S7'!$B$6:$B$19,$A108,'S7'!$E$6:$E$19,"Ambos")+SUMIFS('S8'!$I$6:$I$23,'S8'!$B$6:$B$23,$A108,'S8'!$E$6:$E$23,"Víctor")+SUMIFS('S8'!$I$6:$I$23,'S8'!$B$6:$B$23,$A108,'S8'!$E$6:$E$23,"Ambos")+SUMIFS('S9'!$I$6:$I$15,'S9'!$B$6:$B$15,$A108,'S9'!$E$6:$E$15,"Víctor")+SUMIFS('S9'!$I$6:$I$15,'S9'!$B$6:$B$15,$A108,'S9'!$E$6:$E$15,"Ambos")+SUMIFS('S10'!$I$6:$I$13,'S10'!$B$6:$B$13,$A108,'S10'!$E$6:$E$13,"Víctor")+SUMIFS('S10'!$I$6:$I$13,'S10'!$B$6:$B$13,$A108,'S10'!$E$6:$E$13,"Ambos")+SUMIFS('Holgura'!$I$6:$I$11,'Holgura'!$B$6:$B$11,$A108,'Holgura'!$E$6:$E$11,"Víctor")+SUMIFS('Holgura'!$I$6:$I$11,'Holgura'!$B$6:$B$11,$A108,'Holgura'!$E$6:$E$11,"Ambos")+SUMIFS('Entrega'!$I$6:$I$9,'Entrega'!$B$6:$B$9,$A108,'Entrega'!$E$6:$E$9,"Víctor")+SUMIFS('Entrega'!$I$6:$I$9,'Entrega'!$B$6:$B$9,$A108,'Entrega'!$E$6:$E$9,"Ambos")+SUMIFS('Defensa'!$I$6:$I$10,'Defensa'!$B$6:$B$10,$A108,'Defensa'!$E$6:$E$10,"Víctor")+SUMIFS('Defensa'!$I$6:$I$10,'Defensa'!$B$6:$B$10,$A108,'Defensa'!$E$6:$E$10,"Ambos")</f>
+        <f>SUMIFS('S1'!$I$6:$I$32,'S1'!$B$6:$B$32,$A108,'S1'!$E$6:$E$32,"Víctor")+SUMIFS('S1'!$I$6:$I$32,'S1'!$B$6:$B$32,$A108,'S1'!$E$6:$E$32,"Ambos")+SUMIFS('S2'!$I$6:$I$23,'S2'!$B$6:$B$23,$A108,'S2'!$E$6:$E$23,"Víctor")+SUMIFS('S2'!$I$6:$I$23,'S2'!$B$6:$B$23,$A108,'S2'!$E$6:$E$23,"Ambos")+SUMIFS('S3'!$I$6:$I$24,'S3'!$B$6:$B$24,$A108,'S3'!$E$6:$E$24,"Víctor")+SUMIFS('S3'!$I$6:$I$24,'S3'!$B$6:$B$24,$A108,'S3'!$E$6:$E$24,"Ambos")+SUMIFS('S4'!$I$6:$I$22,'S4'!$B$6:$B$22,$A108,'S4'!$E$6:$E$22,"Víctor")+SUMIFS('S4'!$I$6:$I$22,'S4'!$B$6:$B$22,$A108,'S4'!$E$6:$E$22,"Ambos")+SUMIFS('S5'!$I$6:$I$20,'S5'!$B$6:$B$20,$A108,'S5'!$E$6:$E$20,"Víctor")+SUMIFS('S5'!$I$6:$I$20,'S5'!$B$6:$B$20,$A108,'S5'!$E$6:$E$20,"Ambos")+SUMIFS('S6'!$I$6:$I$17,'S6'!$B$6:$B$17,$A108,'S6'!$E$6:$E$17,"Víctor")+SUMIFS('S6'!$I$6:$I$17,'S6'!$B$6:$B$17,$A108,'S6'!$E$6:$E$17,"Ambos")+SUMIFS('S7'!$I$6:$I$19,'S7'!$B$6:$B$19,$A108,'S7'!$E$6:$E$19,"Víctor")+SUMIFS('S7'!$I$6:$I$19,'S7'!$B$6:$B$19,$A108,'S7'!$E$6:$E$19,"Ambos")+SUMIFS('S8'!$I$6:$I$23,'S8'!$B$6:$B$23,$A108,'S8'!$E$6:$E$23,"Víctor")+SUMIFS('S8'!$I$6:$I$23,'S8'!$B$6:$B$23,$A108,'S8'!$E$6:$E$23,"Ambos")+SUMIFS('S9'!$I$6:$I$15,'S9'!$B$6:$B$15,$A108,'S9'!$E$6:$E$15,"Víctor")+SUMIFS('S9'!$I$6:$I$15,'S9'!$B$6:$B$15,$A108,'S9'!$E$6:$E$15,"Ambos")+SUMIFS('S10'!$I$6:$I$13,'S10'!$B$6:$B$13,$A108,'S10'!$E$6:$E$13,"Víctor")+SUMIFS('S10'!$I$6:$I$13,'S10'!$B$6:$B$13,$A108,'S10'!$E$6:$E$13,"Ambos")+SUMIFS('Holgura'!$I$6:$I$11,'Holgura'!$B$6:$B$11,$A108,'Holgura'!$E$6:$E$11,"Víctor")+SUMIFS('Holgura'!$I$6:$I$11,'Holgura'!$B$6:$B$11,$A108,'Holgura'!$E$6:$E$11,"Ambos")+SUMIFS('Entrega'!$I$6:$I$9,'Entrega'!$B$6:$B$9,$A108,'Entrega'!$E$6:$E$9,"Víctor")+SUMIFS('Entrega'!$I$6:$I$9,'Entrega'!$B$6:$B$9,$A108,'Entrega'!$E$6:$E$9,"Ambos")+SUMIFS('Defensa'!$I$6:$I$10,'Defensa'!$B$6:$B$10,$A108,'Defensa'!$E$6:$E$10,"Víctor")+SUMIFS('Defensa'!$I$6:$I$10,'Defensa'!$B$6:$B$10,$A108,'Defensa'!$E$6:$E$10,"Ambos")</f>
         <v/>
       </c>
       <c r="E108" s="21">
-        <f>SUMIFS('S1'!$I$6:$I$32,'S1'!$B$6:$B$32,$A108,'S1'!$E$6:$E$32,"Diego")+SUMIFS('S1'!$I$6:$I$32,'S1'!$B$6:$B$32,$A108,'S1'!$E$6:$E$32,"Ambos")+SUMIFS('S2'!$I$6:$I$23,'S2'!$B$6:$B$23,$A108,'S2'!$E$6:$E$23,"Diego")+SUMIFS('S2'!$I$6:$I$23,'S2'!$B$6:$B$23,$A108,'S2'!$E$6:$E$23,"Ambos")+SUMIFS('S3'!$I$6:$I$19,'S3'!$B$6:$B$19,$A108,'S3'!$E$6:$E$19,"Diego")+SUMIFS('S3'!$I$6:$I$19,'S3'!$B$6:$B$19,$A108,'S3'!$E$6:$E$19,"Ambos")+SUMIFS('S4'!$I$6:$I$20,'S4'!$B$6:$B$20,$A108,'S4'!$E$6:$E$20,"Diego")+SUMIFS('S4'!$I$6:$I$20,'S4'!$B$6:$B$20,$A108,'S4'!$E$6:$E$20,"Ambos")+SUMIFS('S5'!$I$6:$I$20,'S5'!$B$6:$B$20,$A108,'S5'!$E$6:$E$20,"Diego")+SUMIFS('S5'!$I$6:$I$20,'S5'!$B$6:$B$20,$A108,'S5'!$E$6:$E$20,"Ambos")+SUMIFS('S6'!$I$6:$I$17,'S6'!$B$6:$B$17,$A108,'S6'!$E$6:$E$17,"Diego")+SUMIFS('S6'!$I$6:$I$17,'S6'!$B$6:$B$17,$A108,'S6'!$E$6:$E$17,"Ambos")+SUMIFS('S7'!$I$6:$I$19,'S7'!$B$6:$B$19,$A108,'S7'!$E$6:$E$19,"Diego")+SUMIFS('S7'!$I$6:$I$19,'S7'!$B$6:$B$19,$A108,'S7'!$E$6:$E$19,"Ambos")+SUMIFS('S8'!$I$6:$I$23,'S8'!$B$6:$B$23,$A108,'S8'!$E$6:$E$23,"Diego")+SUMIFS('S8'!$I$6:$I$23,'S8'!$B$6:$B$23,$A108,'S8'!$E$6:$E$23,"Ambos")+SUMIFS('S9'!$I$6:$I$15,'S9'!$B$6:$B$15,$A108,'S9'!$E$6:$E$15,"Diego")+SUMIFS('S9'!$I$6:$I$15,'S9'!$B$6:$B$15,$A108,'S9'!$E$6:$E$15,"Ambos")+SUMIFS('S10'!$I$6:$I$13,'S10'!$B$6:$B$13,$A108,'S10'!$E$6:$E$13,"Diego")+SUMIFS('S10'!$I$6:$I$13,'S10'!$B$6:$B$13,$A108,'S10'!$E$6:$E$13,"Ambos")+SUMIFS('Holgura'!$I$6:$I$11,'Holgura'!$B$6:$B$11,$A108,'Holgura'!$E$6:$E$11,"Diego")+SUMIFS('Holgura'!$I$6:$I$11,'Holgura'!$B$6:$B$11,$A108,'Holgura'!$E$6:$E$11,"Ambos")+SUMIFS('Entrega'!$I$6:$I$9,'Entrega'!$B$6:$B$9,$A108,'Entrega'!$E$6:$E$9,"Diego")+SUMIFS('Entrega'!$I$6:$I$9,'Entrega'!$B$6:$B$9,$A108,'Entrega'!$E$6:$E$9,"Ambos")+SUMIFS('Defensa'!$I$6:$I$10,'Defensa'!$B$6:$B$10,$A108,'Defensa'!$E$6:$E$10,"Diego")+SUMIFS('Defensa'!$I$6:$I$10,'Defensa'!$B$6:$B$10,$A108,'Defensa'!$E$6:$E$10,"Ambos")</f>
+        <f>SUMIFS('S1'!$I$6:$I$32,'S1'!$B$6:$B$32,$A108,'S1'!$E$6:$E$32,"Diego")+SUMIFS('S1'!$I$6:$I$32,'S1'!$B$6:$B$32,$A108,'S1'!$E$6:$E$32,"Ambos")+SUMIFS('S2'!$I$6:$I$23,'S2'!$B$6:$B$23,$A108,'S2'!$E$6:$E$23,"Diego")+SUMIFS('S2'!$I$6:$I$23,'S2'!$B$6:$B$23,$A108,'S2'!$E$6:$E$23,"Ambos")+SUMIFS('S3'!$I$6:$I$24,'S3'!$B$6:$B$24,$A108,'S3'!$E$6:$E$24,"Diego")+SUMIFS('S3'!$I$6:$I$24,'S3'!$B$6:$B$24,$A108,'S3'!$E$6:$E$24,"Ambos")+SUMIFS('S4'!$I$6:$I$22,'S4'!$B$6:$B$22,$A108,'S4'!$E$6:$E$22,"Diego")+SUMIFS('S4'!$I$6:$I$22,'S4'!$B$6:$B$22,$A108,'S4'!$E$6:$E$22,"Ambos")+SUMIFS('S5'!$I$6:$I$20,'S5'!$B$6:$B$20,$A108,'S5'!$E$6:$E$20,"Diego")+SUMIFS('S5'!$I$6:$I$20,'S5'!$B$6:$B$20,$A108,'S5'!$E$6:$E$20,"Ambos")+SUMIFS('S6'!$I$6:$I$17,'S6'!$B$6:$B$17,$A108,'S6'!$E$6:$E$17,"Diego")+SUMIFS('S6'!$I$6:$I$17,'S6'!$B$6:$B$17,$A108,'S6'!$E$6:$E$17,"Ambos")+SUMIFS('S7'!$I$6:$I$19,'S7'!$B$6:$B$19,$A108,'S7'!$E$6:$E$19,"Diego")+SUMIFS('S7'!$I$6:$I$19,'S7'!$B$6:$B$19,$A108,'S7'!$E$6:$E$19,"Ambos")+SUMIFS('S8'!$I$6:$I$23,'S8'!$B$6:$B$23,$A108,'S8'!$E$6:$E$23,"Diego")+SUMIFS('S8'!$I$6:$I$23,'S8'!$B$6:$B$23,$A108,'S8'!$E$6:$E$23,"Ambos")+SUMIFS('S9'!$I$6:$I$15,'S9'!$B$6:$B$15,$A108,'S9'!$E$6:$E$15,"Diego")+SUMIFS('S9'!$I$6:$I$15,'S9'!$B$6:$B$15,$A108,'S9'!$E$6:$E$15,"Ambos")+SUMIFS('S10'!$I$6:$I$13,'S10'!$B$6:$B$13,$A108,'S10'!$E$6:$E$13,"Diego")+SUMIFS('S10'!$I$6:$I$13,'S10'!$B$6:$B$13,$A108,'S10'!$E$6:$E$13,"Ambos")+SUMIFS('Holgura'!$I$6:$I$11,'Holgura'!$B$6:$B$11,$A108,'Holgura'!$E$6:$E$11,"Diego")+SUMIFS('Holgura'!$I$6:$I$11,'Holgura'!$B$6:$B$11,$A108,'Holgura'!$E$6:$E$11,"Ambos")+SUMIFS('Entrega'!$I$6:$I$9,'Entrega'!$B$6:$B$9,$A108,'Entrega'!$E$6:$E$9,"Diego")+SUMIFS('Entrega'!$I$6:$I$9,'Entrega'!$B$6:$B$9,$A108,'Entrega'!$E$6:$E$9,"Ambos")+SUMIFS('Defensa'!$I$6:$I$10,'Defensa'!$B$6:$B$10,$A108,'Defensa'!$E$6:$E$10,"Diego")+SUMIFS('Defensa'!$I$6:$I$10,'Defensa'!$B$6:$B$10,$A108,'Defensa'!$E$6:$E$10,"Ambos")</f>
         <v/>
       </c>
       <c r="F108" s="21">
-        <f>COUNTIFS('S1'!$B$6:$B$32,$A108,'S1'!$E$6:$E$32,"Víctor")+COUNTIFS('S1'!$B$6:$B$32,$A108,'S1'!$E$6:$E$32,"Ambos")+COUNTIFS('S2'!$B$6:$B$23,$A108,'S2'!$E$6:$E$23,"Víctor")+COUNTIFS('S2'!$B$6:$B$23,$A108,'S2'!$E$6:$E$23,"Ambos")+COUNTIFS('S3'!$B$6:$B$19,$A108,'S3'!$E$6:$E$19,"Víctor")+COUNTIFS('S3'!$B$6:$B$19,$A108,'S3'!$E$6:$E$19,"Ambos")+COUNTIFS('S4'!$B$6:$B$20,$A108,'S4'!$E$6:$E$20,"Víctor")+COUNTIFS('S4'!$B$6:$B$20,$A108,'S4'!$E$6:$E$20,"Ambos")+COUNTIFS('S5'!$B$6:$B$20,$A108,'S5'!$E$6:$E$20,"Víctor")+COUNTIFS('S5'!$B$6:$B$20,$A108,'S5'!$E$6:$E$20,"Ambos")+COUNTIFS('S6'!$B$6:$B$17,$A108,'S6'!$E$6:$E$17,"Víctor")+COUNTIFS('S6'!$B$6:$B$17,$A108,'S6'!$E$6:$E$17,"Ambos")+COUNTIFS('S7'!$B$6:$B$19,$A108,'S7'!$E$6:$E$19,"Víctor")+COUNTIFS('S7'!$B$6:$B$19,$A108,'S7'!$E$6:$E$19,"Ambos")+COUNTIFS('S8'!$B$6:$B$23,$A108,'S8'!$E$6:$E$23,"Víctor")+COUNTIFS('S8'!$B$6:$B$23,$A108,'S8'!$E$6:$E$23,"Ambos")+COUNTIFS('S9'!$B$6:$B$15,$A108,'S9'!$E$6:$E$15,"Víctor")+COUNTIFS('S9'!$B$6:$B$15,$A108,'S9'!$E$6:$E$15,"Ambos")+COUNTIFS('S10'!$B$6:$B$13,$A108,'S10'!$E$6:$E$13,"Víctor")+COUNTIFS('S10'!$B$6:$B$13,$A108,'S10'!$E$6:$E$13,"Ambos")+COUNTIFS('Holgura'!$B$6:$B$11,$A108,'Holgura'!$E$6:$E$11,"Víctor")+COUNTIFS('Holgura'!$B$6:$B$11,$A108,'Holgura'!$E$6:$E$11,"Ambos")+COUNTIFS('Entrega'!$B$6:$B$9,$A108,'Entrega'!$E$6:$E$9,"Víctor")+COUNTIFS('Entrega'!$B$6:$B$9,$A108,'Entrega'!$E$6:$E$9,"Ambos")+COUNTIFS('Defensa'!$B$6:$B$10,$A108,'Defensa'!$E$6:$E$10,"Víctor")+COUNTIFS('Defensa'!$B$6:$B$10,$A108,'Defensa'!$E$6:$E$10,"Ambos")</f>
+        <f>COUNTIFS('S1'!$B$6:$B$32,$A108,'S1'!$E$6:$E$32,"Víctor")+COUNTIFS('S1'!$B$6:$B$32,$A108,'S1'!$E$6:$E$32,"Ambos")+COUNTIFS('S2'!$B$6:$B$23,$A108,'S2'!$E$6:$E$23,"Víctor")+COUNTIFS('S2'!$B$6:$B$23,$A108,'S2'!$E$6:$E$23,"Ambos")+COUNTIFS('S3'!$B$6:$B$24,$A108,'S3'!$E$6:$E$24,"Víctor")+COUNTIFS('S3'!$B$6:$B$24,$A108,'S3'!$E$6:$E$24,"Ambos")+COUNTIFS('S4'!$B$6:$B$22,$A108,'S4'!$E$6:$E$22,"Víctor")+COUNTIFS('S4'!$B$6:$B$22,$A108,'S4'!$E$6:$E$22,"Ambos")+COUNTIFS('S5'!$B$6:$B$20,$A108,'S5'!$E$6:$E$20,"Víctor")+COUNTIFS('S5'!$B$6:$B$20,$A108,'S5'!$E$6:$E$20,"Ambos")+COUNTIFS('S6'!$B$6:$B$17,$A108,'S6'!$E$6:$E$17,"Víctor")+COUNTIFS('S6'!$B$6:$B$17,$A108,'S6'!$E$6:$E$17,"Ambos")+COUNTIFS('S7'!$B$6:$B$19,$A108,'S7'!$E$6:$E$19,"Víctor")+COUNTIFS('S7'!$B$6:$B$19,$A108,'S7'!$E$6:$E$19,"Ambos")+COUNTIFS('S8'!$B$6:$B$23,$A108,'S8'!$E$6:$E$23,"Víctor")+COUNTIFS('S8'!$B$6:$B$23,$A108,'S8'!$E$6:$E$23,"Ambos")+COUNTIFS('S9'!$B$6:$B$15,$A108,'S9'!$E$6:$E$15,"Víctor")+COUNTIFS('S9'!$B$6:$B$15,$A108,'S9'!$E$6:$E$15,"Ambos")+COUNTIFS('S10'!$B$6:$B$13,$A108,'S10'!$E$6:$E$13,"Víctor")+COUNTIFS('S10'!$B$6:$B$13,$A108,'S10'!$E$6:$E$13,"Ambos")+COUNTIFS('Holgura'!$B$6:$B$11,$A108,'Holgura'!$E$6:$E$11,"Víctor")+COUNTIFS('Holgura'!$B$6:$B$11,$A108,'Holgura'!$E$6:$E$11,"Ambos")+COUNTIFS('Entrega'!$B$6:$B$9,$A108,'Entrega'!$E$6:$E$9,"Víctor")+COUNTIFS('Entrega'!$B$6:$B$9,$A108,'Entrega'!$E$6:$E$9,"Ambos")+COUNTIFS('Defensa'!$B$6:$B$10,$A108,'Defensa'!$E$6:$E$10,"Víctor")+COUNTIFS('Defensa'!$B$6:$B$10,$A108,'Defensa'!$E$6:$E$10,"Ambos")</f>
         <v/>
       </c>
       <c r="G108" s="21">
-        <f>COUNTIFS('S1'!$B$6:$B$32,$A108,'S1'!$E$6:$E$32,"Diego")+COUNTIFS('S1'!$B$6:$B$32,$A108,'S1'!$E$6:$E$32,"Ambos")+COUNTIFS('S2'!$B$6:$B$23,$A108,'S2'!$E$6:$E$23,"Diego")+COUNTIFS('S2'!$B$6:$B$23,$A108,'S2'!$E$6:$E$23,"Ambos")+COUNTIFS('S3'!$B$6:$B$19,$A108,'S3'!$E$6:$E$19,"Diego")+COUNTIFS('S3'!$B$6:$B$19,$A108,'S3'!$E$6:$E$19,"Ambos")+COUNTIFS('S4'!$B$6:$B$20,$A108,'S4'!$E$6:$E$20,"Diego")+COUNTIFS('S4'!$B$6:$B$20,$A108,'S4'!$E$6:$E$20,"Ambos")+COUNTIFS('S5'!$B$6:$B$20,$A108,'S5'!$E$6:$E$20,"Diego")+COUNTIFS('S5'!$B$6:$B$20,$A108,'S5'!$E$6:$E$20,"Ambos")+COUNTIFS('S6'!$B$6:$B$17,$A108,'S6'!$E$6:$E$17,"Diego")+COUNTIFS('S6'!$B$6:$B$17,$A108,'S6'!$E$6:$E$17,"Ambos")+COUNTIFS('S7'!$B$6:$B$19,$A108,'S7'!$E$6:$E$19,"Diego")+COUNTIFS('S7'!$B$6:$B$19,$A108,'S7'!$E$6:$E$19,"Ambos")+COUNTIFS('S8'!$B$6:$B$23,$A108,'S8'!$E$6:$E$23,"Diego")+COUNTIFS('S8'!$B$6:$B$23,$A108,'S8'!$E$6:$E$23,"Ambos")+COUNTIFS('S9'!$B$6:$B$15,$A108,'S9'!$E$6:$E$15,"Diego")+COUNTIFS('S9'!$B$6:$B$15,$A108,'S9'!$E$6:$E$15,"Ambos")+COUNTIFS('S10'!$B$6:$B$13,$A108,'S10'!$E$6:$E$13,"Diego")+COUNTIFS('S10'!$B$6:$B$13,$A108,'S10'!$E$6:$E$13,"Ambos")+COUNTIFS('Holgura'!$B$6:$B$11,$A108,'Holgura'!$E$6:$E$11,"Diego")+COUNTIFS('Holgura'!$B$6:$B$11,$A108,'Holgura'!$E$6:$E$11,"Ambos")+COUNTIFS('Entrega'!$B$6:$B$9,$A108,'Entrega'!$E$6:$E$9,"Diego")+COUNTIFS('Entrega'!$B$6:$B$9,$A108,'Entrega'!$E$6:$E$9,"Ambos")+COUNTIFS('Defensa'!$B$6:$B$10,$A108,'Defensa'!$E$6:$E$10,"Diego")+COUNTIFS('Defensa'!$B$6:$B$10,$A108,'Defensa'!$E$6:$E$10,"Ambos")</f>
+        <f>COUNTIFS('S1'!$B$6:$B$32,$A108,'S1'!$E$6:$E$32,"Diego")+COUNTIFS('S1'!$B$6:$B$32,$A108,'S1'!$E$6:$E$32,"Ambos")+COUNTIFS('S2'!$B$6:$B$23,$A108,'S2'!$E$6:$E$23,"Diego")+COUNTIFS('S2'!$B$6:$B$23,$A108,'S2'!$E$6:$E$23,"Ambos")+COUNTIFS('S3'!$B$6:$B$24,$A108,'S3'!$E$6:$E$24,"Diego")+COUNTIFS('S3'!$B$6:$B$24,$A108,'S3'!$E$6:$E$24,"Ambos")+COUNTIFS('S4'!$B$6:$B$22,$A108,'S4'!$E$6:$E$22,"Diego")+COUNTIFS('S4'!$B$6:$B$22,$A108,'S4'!$E$6:$E$22,"Ambos")+COUNTIFS('S5'!$B$6:$B$20,$A108,'S5'!$E$6:$E$20,"Diego")+COUNTIFS('S5'!$B$6:$B$20,$A108,'S5'!$E$6:$E$20,"Ambos")+COUNTIFS('S6'!$B$6:$B$17,$A108,'S6'!$E$6:$E$17,"Diego")+COUNTIFS('S6'!$B$6:$B$17,$A108,'S6'!$E$6:$E$17,"Ambos")+COUNTIFS('S7'!$B$6:$B$19,$A108,'S7'!$E$6:$E$19,"Diego")+COUNTIFS('S7'!$B$6:$B$19,$A108,'S7'!$E$6:$E$19,"Ambos")+COUNTIFS('S8'!$B$6:$B$23,$A108,'S8'!$E$6:$E$23,"Diego")+COUNTIFS('S8'!$B$6:$B$23,$A108,'S8'!$E$6:$E$23,"Ambos")+COUNTIFS('S9'!$B$6:$B$15,$A108,'S9'!$E$6:$E$15,"Diego")+COUNTIFS('S9'!$B$6:$B$15,$A108,'S9'!$E$6:$E$15,"Ambos")+COUNTIFS('S10'!$B$6:$B$13,$A108,'S10'!$E$6:$E$13,"Diego")+COUNTIFS('S10'!$B$6:$B$13,$A108,'S10'!$E$6:$E$13,"Ambos")+COUNTIFS('Holgura'!$B$6:$B$11,$A108,'Holgura'!$E$6:$E$11,"Diego")+COUNTIFS('Holgura'!$B$6:$B$11,$A108,'Holgura'!$E$6:$E$11,"Ambos")+COUNTIFS('Entrega'!$B$6:$B$9,$A108,'Entrega'!$E$6:$E$9,"Diego")+COUNTIFS('Entrega'!$B$6:$B$9,$A108,'Entrega'!$E$6:$E$9,"Ambos")+COUNTIFS('Defensa'!$B$6:$B$10,$A108,'Defensa'!$E$6:$E$10,"Diego")+COUNTIFS('Defensa'!$B$6:$B$10,$A108,'Defensa'!$E$6:$E$10,"Ambos")</f>
         <v/>
       </c>
     </row>
@@ -11696,19 +11717,19 @@
         <v/>
       </c>
       <c r="D109" s="21">
-        <f>SUMIFS('S1'!$I$6:$I$32,'S1'!$B$6:$B$32,$A109,'S1'!$E$6:$E$32,"Víctor")+SUMIFS('S1'!$I$6:$I$32,'S1'!$B$6:$B$32,$A109,'S1'!$E$6:$E$32,"Ambos")+SUMIFS('S2'!$I$6:$I$23,'S2'!$B$6:$B$23,$A109,'S2'!$E$6:$E$23,"Víctor")+SUMIFS('S2'!$I$6:$I$23,'S2'!$B$6:$B$23,$A109,'S2'!$E$6:$E$23,"Ambos")+SUMIFS('S3'!$I$6:$I$19,'S3'!$B$6:$B$19,$A109,'S3'!$E$6:$E$19,"Víctor")+SUMIFS('S3'!$I$6:$I$19,'S3'!$B$6:$B$19,$A109,'S3'!$E$6:$E$19,"Ambos")+SUMIFS('S4'!$I$6:$I$20,'S4'!$B$6:$B$20,$A109,'S4'!$E$6:$E$20,"Víctor")+SUMIFS('S4'!$I$6:$I$20,'S4'!$B$6:$B$20,$A109,'S4'!$E$6:$E$20,"Ambos")+SUMIFS('S5'!$I$6:$I$20,'S5'!$B$6:$B$20,$A109,'S5'!$E$6:$E$20,"Víctor")+SUMIFS('S5'!$I$6:$I$20,'S5'!$B$6:$B$20,$A109,'S5'!$E$6:$E$20,"Ambos")+SUMIFS('S6'!$I$6:$I$17,'S6'!$B$6:$B$17,$A109,'S6'!$E$6:$E$17,"Víctor")+SUMIFS('S6'!$I$6:$I$17,'S6'!$B$6:$B$17,$A109,'S6'!$E$6:$E$17,"Ambos")+SUMIFS('S7'!$I$6:$I$19,'S7'!$B$6:$B$19,$A109,'S7'!$E$6:$E$19,"Víctor")+SUMIFS('S7'!$I$6:$I$19,'S7'!$B$6:$B$19,$A109,'S7'!$E$6:$E$19,"Ambos")+SUMIFS('S8'!$I$6:$I$23,'S8'!$B$6:$B$23,$A109,'S8'!$E$6:$E$23,"Víctor")+SUMIFS('S8'!$I$6:$I$23,'S8'!$B$6:$B$23,$A109,'S8'!$E$6:$E$23,"Ambos")+SUMIFS('S9'!$I$6:$I$15,'S9'!$B$6:$B$15,$A109,'S9'!$E$6:$E$15,"Víctor")+SUMIFS('S9'!$I$6:$I$15,'S9'!$B$6:$B$15,$A109,'S9'!$E$6:$E$15,"Ambos")+SUMIFS('S10'!$I$6:$I$13,'S10'!$B$6:$B$13,$A109,'S10'!$E$6:$E$13,"Víctor")+SUMIFS('S10'!$I$6:$I$13,'S10'!$B$6:$B$13,$A109,'S10'!$E$6:$E$13,"Ambos")+SUMIFS('Holgura'!$I$6:$I$11,'Holgura'!$B$6:$B$11,$A109,'Holgura'!$E$6:$E$11,"Víctor")+SUMIFS('Holgura'!$I$6:$I$11,'Holgura'!$B$6:$B$11,$A109,'Holgura'!$E$6:$E$11,"Ambos")+SUMIFS('Entrega'!$I$6:$I$9,'Entrega'!$B$6:$B$9,$A109,'Entrega'!$E$6:$E$9,"Víctor")+SUMIFS('Entrega'!$I$6:$I$9,'Entrega'!$B$6:$B$9,$A109,'Entrega'!$E$6:$E$9,"Ambos")+SUMIFS('Defensa'!$I$6:$I$10,'Defensa'!$B$6:$B$10,$A109,'Defensa'!$E$6:$E$10,"Víctor")+SUMIFS('Defensa'!$I$6:$I$10,'Defensa'!$B$6:$B$10,$A109,'Defensa'!$E$6:$E$10,"Ambos")</f>
+        <f>SUMIFS('S1'!$I$6:$I$32,'S1'!$B$6:$B$32,$A109,'S1'!$E$6:$E$32,"Víctor")+SUMIFS('S1'!$I$6:$I$32,'S1'!$B$6:$B$32,$A109,'S1'!$E$6:$E$32,"Ambos")+SUMIFS('S2'!$I$6:$I$23,'S2'!$B$6:$B$23,$A109,'S2'!$E$6:$E$23,"Víctor")+SUMIFS('S2'!$I$6:$I$23,'S2'!$B$6:$B$23,$A109,'S2'!$E$6:$E$23,"Ambos")+SUMIFS('S3'!$I$6:$I$24,'S3'!$B$6:$B$24,$A109,'S3'!$E$6:$E$24,"Víctor")+SUMIFS('S3'!$I$6:$I$24,'S3'!$B$6:$B$24,$A109,'S3'!$E$6:$E$24,"Ambos")+SUMIFS('S4'!$I$6:$I$22,'S4'!$B$6:$B$22,$A109,'S4'!$E$6:$E$22,"Víctor")+SUMIFS('S4'!$I$6:$I$22,'S4'!$B$6:$B$22,$A109,'S4'!$E$6:$E$22,"Ambos")+SUMIFS('S5'!$I$6:$I$20,'S5'!$B$6:$B$20,$A109,'S5'!$E$6:$E$20,"Víctor")+SUMIFS('S5'!$I$6:$I$20,'S5'!$B$6:$B$20,$A109,'S5'!$E$6:$E$20,"Ambos")+SUMIFS('S6'!$I$6:$I$17,'S6'!$B$6:$B$17,$A109,'S6'!$E$6:$E$17,"Víctor")+SUMIFS('S6'!$I$6:$I$17,'S6'!$B$6:$B$17,$A109,'S6'!$E$6:$E$17,"Ambos")+SUMIFS('S7'!$I$6:$I$19,'S7'!$B$6:$B$19,$A109,'S7'!$E$6:$E$19,"Víctor")+SUMIFS('S7'!$I$6:$I$19,'S7'!$B$6:$B$19,$A109,'S7'!$E$6:$E$19,"Ambos")+SUMIFS('S8'!$I$6:$I$23,'S8'!$B$6:$B$23,$A109,'S8'!$E$6:$E$23,"Víctor")+SUMIFS('S8'!$I$6:$I$23,'S8'!$B$6:$B$23,$A109,'S8'!$E$6:$E$23,"Ambos")+SUMIFS('S9'!$I$6:$I$15,'S9'!$B$6:$B$15,$A109,'S9'!$E$6:$E$15,"Víctor")+SUMIFS('S9'!$I$6:$I$15,'S9'!$B$6:$B$15,$A109,'S9'!$E$6:$E$15,"Ambos")+SUMIFS('S10'!$I$6:$I$13,'S10'!$B$6:$B$13,$A109,'S10'!$E$6:$E$13,"Víctor")+SUMIFS('S10'!$I$6:$I$13,'S10'!$B$6:$B$13,$A109,'S10'!$E$6:$E$13,"Ambos")+SUMIFS('Holgura'!$I$6:$I$11,'Holgura'!$B$6:$B$11,$A109,'Holgura'!$E$6:$E$11,"Víctor")+SUMIFS('Holgura'!$I$6:$I$11,'Holgura'!$B$6:$B$11,$A109,'Holgura'!$E$6:$E$11,"Ambos")+SUMIFS('Entrega'!$I$6:$I$9,'Entrega'!$B$6:$B$9,$A109,'Entrega'!$E$6:$E$9,"Víctor")+SUMIFS('Entrega'!$I$6:$I$9,'Entrega'!$B$6:$B$9,$A109,'Entrega'!$E$6:$E$9,"Ambos")+SUMIFS('Defensa'!$I$6:$I$10,'Defensa'!$B$6:$B$10,$A109,'Defensa'!$E$6:$E$10,"Víctor")+SUMIFS('Defensa'!$I$6:$I$10,'Defensa'!$B$6:$B$10,$A109,'Defensa'!$E$6:$E$10,"Ambos")</f>
         <v/>
       </c>
       <c r="E109" s="21">
-        <f>SUMIFS('S1'!$I$6:$I$32,'S1'!$B$6:$B$32,$A109,'S1'!$E$6:$E$32,"Diego")+SUMIFS('S1'!$I$6:$I$32,'S1'!$B$6:$B$32,$A109,'S1'!$E$6:$E$32,"Ambos")+SUMIFS('S2'!$I$6:$I$23,'S2'!$B$6:$B$23,$A109,'S2'!$E$6:$E$23,"Diego")+SUMIFS('S2'!$I$6:$I$23,'S2'!$B$6:$B$23,$A109,'S2'!$E$6:$E$23,"Ambos")+SUMIFS('S3'!$I$6:$I$19,'S3'!$B$6:$B$19,$A109,'S3'!$E$6:$E$19,"Diego")+SUMIFS('S3'!$I$6:$I$19,'S3'!$B$6:$B$19,$A109,'S3'!$E$6:$E$19,"Ambos")+SUMIFS('S4'!$I$6:$I$20,'S4'!$B$6:$B$20,$A109,'S4'!$E$6:$E$20,"Diego")+SUMIFS('S4'!$I$6:$I$20,'S4'!$B$6:$B$20,$A109,'S4'!$E$6:$E$20,"Ambos")+SUMIFS('S5'!$I$6:$I$20,'S5'!$B$6:$B$20,$A109,'S5'!$E$6:$E$20,"Diego")+SUMIFS('S5'!$I$6:$I$20,'S5'!$B$6:$B$20,$A109,'S5'!$E$6:$E$20,"Ambos")+SUMIFS('S6'!$I$6:$I$17,'S6'!$B$6:$B$17,$A109,'S6'!$E$6:$E$17,"Diego")+SUMIFS('S6'!$I$6:$I$17,'S6'!$B$6:$B$17,$A109,'S6'!$E$6:$E$17,"Ambos")+SUMIFS('S7'!$I$6:$I$19,'S7'!$B$6:$B$19,$A109,'S7'!$E$6:$E$19,"Diego")+SUMIFS('S7'!$I$6:$I$19,'S7'!$B$6:$B$19,$A109,'S7'!$E$6:$E$19,"Ambos")+SUMIFS('S8'!$I$6:$I$23,'S8'!$B$6:$B$23,$A109,'S8'!$E$6:$E$23,"Diego")+SUMIFS('S8'!$I$6:$I$23,'S8'!$B$6:$B$23,$A109,'S8'!$E$6:$E$23,"Ambos")+SUMIFS('S9'!$I$6:$I$15,'S9'!$B$6:$B$15,$A109,'S9'!$E$6:$E$15,"Diego")+SUMIFS('S9'!$I$6:$I$15,'S9'!$B$6:$B$15,$A109,'S9'!$E$6:$E$15,"Ambos")+SUMIFS('S10'!$I$6:$I$13,'S10'!$B$6:$B$13,$A109,'S10'!$E$6:$E$13,"Diego")+SUMIFS('S10'!$I$6:$I$13,'S10'!$B$6:$B$13,$A109,'S10'!$E$6:$E$13,"Ambos")+SUMIFS('Holgura'!$I$6:$I$11,'Holgura'!$B$6:$B$11,$A109,'Holgura'!$E$6:$E$11,"Diego")+SUMIFS('Holgura'!$I$6:$I$11,'Holgura'!$B$6:$B$11,$A109,'Holgura'!$E$6:$E$11,"Ambos")+SUMIFS('Entrega'!$I$6:$I$9,'Entrega'!$B$6:$B$9,$A109,'Entrega'!$E$6:$E$9,"Diego")+SUMIFS('Entrega'!$I$6:$I$9,'Entrega'!$B$6:$B$9,$A109,'Entrega'!$E$6:$E$9,"Ambos")+SUMIFS('Defensa'!$I$6:$I$10,'Defensa'!$B$6:$B$10,$A109,'Defensa'!$E$6:$E$10,"Diego")+SUMIFS('Defensa'!$I$6:$I$10,'Defensa'!$B$6:$B$10,$A109,'Defensa'!$E$6:$E$10,"Ambos")</f>
+        <f>SUMIFS('S1'!$I$6:$I$32,'S1'!$B$6:$B$32,$A109,'S1'!$E$6:$E$32,"Diego")+SUMIFS('S1'!$I$6:$I$32,'S1'!$B$6:$B$32,$A109,'S1'!$E$6:$E$32,"Ambos")+SUMIFS('S2'!$I$6:$I$23,'S2'!$B$6:$B$23,$A109,'S2'!$E$6:$E$23,"Diego")+SUMIFS('S2'!$I$6:$I$23,'S2'!$B$6:$B$23,$A109,'S2'!$E$6:$E$23,"Ambos")+SUMIFS('S3'!$I$6:$I$24,'S3'!$B$6:$B$24,$A109,'S3'!$E$6:$E$24,"Diego")+SUMIFS('S3'!$I$6:$I$24,'S3'!$B$6:$B$24,$A109,'S3'!$E$6:$E$24,"Ambos")+SUMIFS('S4'!$I$6:$I$22,'S4'!$B$6:$B$22,$A109,'S4'!$E$6:$E$22,"Diego")+SUMIFS('S4'!$I$6:$I$22,'S4'!$B$6:$B$22,$A109,'S4'!$E$6:$E$22,"Ambos")+SUMIFS('S5'!$I$6:$I$20,'S5'!$B$6:$B$20,$A109,'S5'!$E$6:$E$20,"Diego")+SUMIFS('S5'!$I$6:$I$20,'S5'!$B$6:$B$20,$A109,'S5'!$E$6:$E$20,"Ambos")+SUMIFS('S6'!$I$6:$I$17,'S6'!$B$6:$B$17,$A109,'S6'!$E$6:$E$17,"Diego")+SUMIFS('S6'!$I$6:$I$17,'S6'!$B$6:$B$17,$A109,'S6'!$E$6:$E$17,"Ambos")+SUMIFS('S7'!$I$6:$I$19,'S7'!$B$6:$B$19,$A109,'S7'!$E$6:$E$19,"Diego")+SUMIFS('S7'!$I$6:$I$19,'S7'!$B$6:$B$19,$A109,'S7'!$E$6:$E$19,"Ambos")+SUMIFS('S8'!$I$6:$I$23,'S8'!$B$6:$B$23,$A109,'S8'!$E$6:$E$23,"Diego")+SUMIFS('S8'!$I$6:$I$23,'S8'!$B$6:$B$23,$A109,'S8'!$E$6:$E$23,"Ambos")+SUMIFS('S9'!$I$6:$I$15,'S9'!$B$6:$B$15,$A109,'S9'!$E$6:$E$15,"Diego")+SUMIFS('S9'!$I$6:$I$15,'S9'!$B$6:$B$15,$A109,'S9'!$E$6:$E$15,"Ambos")+SUMIFS('S10'!$I$6:$I$13,'S10'!$B$6:$B$13,$A109,'S10'!$E$6:$E$13,"Diego")+SUMIFS('S10'!$I$6:$I$13,'S10'!$B$6:$B$13,$A109,'S10'!$E$6:$E$13,"Ambos")+SUMIFS('Holgura'!$I$6:$I$11,'Holgura'!$B$6:$B$11,$A109,'Holgura'!$E$6:$E$11,"Diego")+SUMIFS('Holgura'!$I$6:$I$11,'Holgura'!$B$6:$B$11,$A109,'Holgura'!$E$6:$E$11,"Ambos")+SUMIFS('Entrega'!$I$6:$I$9,'Entrega'!$B$6:$B$9,$A109,'Entrega'!$E$6:$E$9,"Diego")+SUMIFS('Entrega'!$I$6:$I$9,'Entrega'!$B$6:$B$9,$A109,'Entrega'!$E$6:$E$9,"Ambos")+SUMIFS('Defensa'!$I$6:$I$10,'Defensa'!$B$6:$B$10,$A109,'Defensa'!$E$6:$E$10,"Diego")+SUMIFS('Defensa'!$I$6:$I$10,'Defensa'!$B$6:$B$10,$A109,'Defensa'!$E$6:$E$10,"Ambos")</f>
         <v/>
       </c>
       <c r="F109" s="21">
-        <f>COUNTIFS('S1'!$B$6:$B$32,$A109,'S1'!$E$6:$E$32,"Víctor")+COUNTIFS('S1'!$B$6:$B$32,$A109,'S1'!$E$6:$E$32,"Ambos")+COUNTIFS('S2'!$B$6:$B$23,$A109,'S2'!$E$6:$E$23,"Víctor")+COUNTIFS('S2'!$B$6:$B$23,$A109,'S2'!$E$6:$E$23,"Ambos")+COUNTIFS('S3'!$B$6:$B$19,$A109,'S3'!$E$6:$E$19,"Víctor")+COUNTIFS('S3'!$B$6:$B$19,$A109,'S3'!$E$6:$E$19,"Ambos")+COUNTIFS('S4'!$B$6:$B$20,$A109,'S4'!$E$6:$E$20,"Víctor")+COUNTIFS('S4'!$B$6:$B$20,$A109,'S4'!$E$6:$E$20,"Ambos")+COUNTIFS('S5'!$B$6:$B$20,$A109,'S5'!$E$6:$E$20,"Víctor")+COUNTIFS('S5'!$B$6:$B$20,$A109,'S5'!$E$6:$E$20,"Ambos")+COUNTIFS('S6'!$B$6:$B$17,$A109,'S6'!$E$6:$E$17,"Víctor")+COUNTIFS('S6'!$B$6:$B$17,$A109,'S6'!$E$6:$E$17,"Ambos")+COUNTIFS('S7'!$B$6:$B$19,$A109,'S7'!$E$6:$E$19,"Víctor")+COUNTIFS('S7'!$B$6:$B$19,$A109,'S7'!$E$6:$E$19,"Ambos")+COUNTIFS('S8'!$B$6:$B$23,$A109,'S8'!$E$6:$E$23,"Víctor")+COUNTIFS('S8'!$B$6:$B$23,$A109,'S8'!$E$6:$E$23,"Ambos")+COUNTIFS('S9'!$B$6:$B$15,$A109,'S9'!$E$6:$E$15,"Víctor")+COUNTIFS('S9'!$B$6:$B$15,$A109,'S9'!$E$6:$E$15,"Ambos")+COUNTIFS('S10'!$B$6:$B$13,$A109,'S10'!$E$6:$E$13,"Víctor")+COUNTIFS('S10'!$B$6:$B$13,$A109,'S10'!$E$6:$E$13,"Ambos")+COUNTIFS('Holgura'!$B$6:$B$11,$A109,'Holgura'!$E$6:$E$11,"Víctor")+COUNTIFS('Holgura'!$B$6:$B$11,$A109,'Holgura'!$E$6:$E$11,"Ambos")+COUNTIFS('Entrega'!$B$6:$B$9,$A109,'Entrega'!$E$6:$E$9,"Víctor")+COUNTIFS('Entrega'!$B$6:$B$9,$A109,'Entrega'!$E$6:$E$9,"Ambos")+COUNTIFS('Defensa'!$B$6:$B$10,$A109,'Defensa'!$E$6:$E$10,"Víctor")+COUNTIFS('Defensa'!$B$6:$B$10,$A109,'Defensa'!$E$6:$E$10,"Ambos")</f>
+        <f>COUNTIFS('S1'!$B$6:$B$32,$A109,'S1'!$E$6:$E$32,"Víctor")+COUNTIFS('S1'!$B$6:$B$32,$A109,'S1'!$E$6:$E$32,"Ambos")+COUNTIFS('S2'!$B$6:$B$23,$A109,'S2'!$E$6:$E$23,"Víctor")+COUNTIFS('S2'!$B$6:$B$23,$A109,'S2'!$E$6:$E$23,"Ambos")+COUNTIFS('S3'!$B$6:$B$24,$A109,'S3'!$E$6:$E$24,"Víctor")+COUNTIFS('S3'!$B$6:$B$24,$A109,'S3'!$E$6:$E$24,"Ambos")+COUNTIFS('S4'!$B$6:$B$22,$A109,'S4'!$E$6:$E$22,"Víctor")+COUNTIFS('S4'!$B$6:$B$22,$A109,'S4'!$E$6:$E$22,"Ambos")+COUNTIFS('S5'!$B$6:$B$20,$A109,'S5'!$E$6:$E$20,"Víctor")+COUNTIFS('S5'!$B$6:$B$20,$A109,'S5'!$E$6:$E$20,"Ambos")+COUNTIFS('S6'!$B$6:$B$17,$A109,'S6'!$E$6:$E$17,"Víctor")+COUNTIFS('S6'!$B$6:$B$17,$A109,'S6'!$E$6:$E$17,"Ambos")+COUNTIFS('S7'!$B$6:$B$19,$A109,'S7'!$E$6:$E$19,"Víctor")+COUNTIFS('S7'!$B$6:$B$19,$A109,'S7'!$E$6:$E$19,"Ambos")+COUNTIFS('S8'!$B$6:$B$23,$A109,'S8'!$E$6:$E$23,"Víctor")+COUNTIFS('S8'!$B$6:$B$23,$A109,'S8'!$E$6:$E$23,"Ambos")+COUNTIFS('S9'!$B$6:$B$15,$A109,'S9'!$E$6:$E$15,"Víctor")+COUNTIFS('S9'!$B$6:$B$15,$A109,'S9'!$E$6:$E$15,"Ambos")+COUNTIFS('S10'!$B$6:$B$13,$A109,'S10'!$E$6:$E$13,"Víctor")+COUNTIFS('S10'!$B$6:$B$13,$A109,'S10'!$E$6:$E$13,"Ambos")+COUNTIFS('Holgura'!$B$6:$B$11,$A109,'Holgura'!$E$6:$E$11,"Víctor")+COUNTIFS('Holgura'!$B$6:$B$11,$A109,'Holgura'!$E$6:$E$11,"Ambos")+COUNTIFS('Entrega'!$B$6:$B$9,$A109,'Entrega'!$E$6:$E$9,"Víctor")+COUNTIFS('Entrega'!$B$6:$B$9,$A109,'Entrega'!$E$6:$E$9,"Ambos")+COUNTIFS('Defensa'!$B$6:$B$10,$A109,'Defensa'!$E$6:$E$10,"Víctor")+COUNTIFS('Defensa'!$B$6:$B$10,$A109,'Defensa'!$E$6:$E$10,"Ambos")</f>
         <v/>
       </c>
       <c r="G109" s="21">
-        <f>COUNTIFS('S1'!$B$6:$B$32,$A109,'S1'!$E$6:$E$32,"Diego")+COUNTIFS('S1'!$B$6:$B$32,$A109,'S1'!$E$6:$E$32,"Ambos")+COUNTIFS('S2'!$B$6:$B$23,$A109,'S2'!$E$6:$E$23,"Diego")+COUNTIFS('S2'!$B$6:$B$23,$A109,'S2'!$E$6:$E$23,"Ambos")+COUNTIFS('S3'!$B$6:$B$19,$A109,'S3'!$E$6:$E$19,"Diego")+COUNTIFS('S3'!$B$6:$B$19,$A109,'S3'!$E$6:$E$19,"Ambos")+COUNTIFS('S4'!$B$6:$B$20,$A109,'S4'!$E$6:$E$20,"Diego")+COUNTIFS('S4'!$B$6:$B$20,$A109,'S4'!$E$6:$E$20,"Ambos")+COUNTIFS('S5'!$B$6:$B$20,$A109,'S5'!$E$6:$E$20,"Diego")+COUNTIFS('S5'!$B$6:$B$20,$A109,'S5'!$E$6:$E$20,"Ambos")+COUNTIFS('S6'!$B$6:$B$17,$A109,'S6'!$E$6:$E$17,"Diego")+COUNTIFS('S6'!$B$6:$B$17,$A109,'S6'!$E$6:$E$17,"Ambos")+COUNTIFS('S7'!$B$6:$B$19,$A109,'S7'!$E$6:$E$19,"Diego")+COUNTIFS('S7'!$B$6:$B$19,$A109,'S7'!$E$6:$E$19,"Ambos")+COUNTIFS('S8'!$B$6:$B$23,$A109,'S8'!$E$6:$E$23,"Diego")+COUNTIFS('S8'!$B$6:$B$23,$A109,'S8'!$E$6:$E$23,"Ambos")+COUNTIFS('S9'!$B$6:$B$15,$A109,'S9'!$E$6:$E$15,"Diego")+COUNTIFS('S9'!$B$6:$B$15,$A109,'S9'!$E$6:$E$15,"Ambos")+COUNTIFS('S10'!$B$6:$B$13,$A109,'S10'!$E$6:$E$13,"Diego")+COUNTIFS('S10'!$B$6:$B$13,$A109,'S10'!$E$6:$E$13,"Ambos")+COUNTIFS('Holgura'!$B$6:$B$11,$A109,'Holgura'!$E$6:$E$11,"Diego")+COUNTIFS('Holgura'!$B$6:$B$11,$A109,'Holgura'!$E$6:$E$11,"Ambos")+COUNTIFS('Entrega'!$B$6:$B$9,$A109,'Entrega'!$E$6:$E$9,"Diego")+COUNTIFS('Entrega'!$B$6:$B$9,$A109,'Entrega'!$E$6:$E$9,"Ambos")+COUNTIFS('Defensa'!$B$6:$B$10,$A109,'Defensa'!$E$6:$E$10,"Diego")+COUNTIFS('Defensa'!$B$6:$B$10,$A109,'Defensa'!$E$6:$E$10,"Ambos")</f>
+        <f>COUNTIFS('S1'!$B$6:$B$32,$A109,'S1'!$E$6:$E$32,"Diego")+COUNTIFS('S1'!$B$6:$B$32,$A109,'S1'!$E$6:$E$32,"Ambos")+COUNTIFS('S2'!$B$6:$B$23,$A109,'S2'!$E$6:$E$23,"Diego")+COUNTIFS('S2'!$B$6:$B$23,$A109,'S2'!$E$6:$E$23,"Ambos")+COUNTIFS('S3'!$B$6:$B$24,$A109,'S3'!$E$6:$E$24,"Diego")+COUNTIFS('S3'!$B$6:$B$24,$A109,'S3'!$E$6:$E$24,"Ambos")+COUNTIFS('S4'!$B$6:$B$22,$A109,'S4'!$E$6:$E$22,"Diego")+COUNTIFS('S4'!$B$6:$B$22,$A109,'S4'!$E$6:$E$22,"Ambos")+COUNTIFS('S5'!$B$6:$B$20,$A109,'S5'!$E$6:$E$20,"Diego")+COUNTIFS('S5'!$B$6:$B$20,$A109,'S5'!$E$6:$E$20,"Ambos")+COUNTIFS('S6'!$B$6:$B$17,$A109,'S6'!$E$6:$E$17,"Diego")+COUNTIFS('S6'!$B$6:$B$17,$A109,'S6'!$E$6:$E$17,"Ambos")+COUNTIFS('S7'!$B$6:$B$19,$A109,'S7'!$E$6:$E$19,"Diego")+COUNTIFS('S7'!$B$6:$B$19,$A109,'S7'!$E$6:$E$19,"Ambos")+COUNTIFS('S8'!$B$6:$B$23,$A109,'S8'!$E$6:$E$23,"Diego")+COUNTIFS('S8'!$B$6:$B$23,$A109,'S8'!$E$6:$E$23,"Ambos")+COUNTIFS('S9'!$B$6:$B$15,$A109,'S9'!$E$6:$E$15,"Diego")+COUNTIFS('S9'!$B$6:$B$15,$A109,'S9'!$E$6:$E$15,"Ambos")+COUNTIFS('S10'!$B$6:$B$13,$A109,'S10'!$E$6:$E$13,"Diego")+COUNTIFS('S10'!$B$6:$B$13,$A109,'S10'!$E$6:$E$13,"Ambos")+COUNTIFS('Holgura'!$B$6:$B$11,$A109,'Holgura'!$E$6:$E$11,"Diego")+COUNTIFS('Holgura'!$B$6:$B$11,$A109,'Holgura'!$E$6:$E$11,"Ambos")+COUNTIFS('Entrega'!$B$6:$B$9,$A109,'Entrega'!$E$6:$E$9,"Diego")+COUNTIFS('Entrega'!$B$6:$B$9,$A109,'Entrega'!$E$6:$E$9,"Ambos")+COUNTIFS('Defensa'!$B$6:$B$10,$A109,'Defensa'!$E$6:$E$10,"Diego")+COUNTIFS('Defensa'!$B$6:$B$10,$A109,'Defensa'!$E$6:$E$10,"Ambos")</f>
         <v/>
       </c>
     </row>
@@ -11725,19 +11746,19 @@
         <v/>
       </c>
       <c r="D110" s="21">
-        <f>SUMIFS('S1'!$I$6:$I$32,'S1'!$B$6:$B$32,$A110,'S1'!$E$6:$E$32,"Víctor")+SUMIFS('S1'!$I$6:$I$32,'S1'!$B$6:$B$32,$A110,'S1'!$E$6:$E$32,"Ambos")+SUMIFS('S2'!$I$6:$I$23,'S2'!$B$6:$B$23,$A110,'S2'!$E$6:$E$23,"Víctor")+SUMIFS('S2'!$I$6:$I$23,'S2'!$B$6:$B$23,$A110,'S2'!$E$6:$E$23,"Ambos")+SUMIFS('S3'!$I$6:$I$19,'S3'!$B$6:$B$19,$A110,'S3'!$E$6:$E$19,"Víctor")+SUMIFS('S3'!$I$6:$I$19,'S3'!$B$6:$B$19,$A110,'S3'!$E$6:$E$19,"Ambos")+SUMIFS('S4'!$I$6:$I$20,'S4'!$B$6:$B$20,$A110,'S4'!$E$6:$E$20,"Víctor")+SUMIFS('S4'!$I$6:$I$20,'S4'!$B$6:$B$20,$A110,'S4'!$E$6:$E$20,"Ambos")+SUMIFS('S5'!$I$6:$I$20,'S5'!$B$6:$B$20,$A110,'S5'!$E$6:$E$20,"Víctor")+SUMIFS('S5'!$I$6:$I$20,'S5'!$B$6:$B$20,$A110,'S5'!$E$6:$E$20,"Ambos")+SUMIFS('S6'!$I$6:$I$17,'S6'!$B$6:$B$17,$A110,'S6'!$E$6:$E$17,"Víctor")+SUMIFS('S6'!$I$6:$I$17,'S6'!$B$6:$B$17,$A110,'S6'!$E$6:$E$17,"Ambos")+SUMIFS('S7'!$I$6:$I$19,'S7'!$B$6:$B$19,$A110,'S7'!$E$6:$E$19,"Víctor")+SUMIFS('S7'!$I$6:$I$19,'S7'!$B$6:$B$19,$A110,'S7'!$E$6:$E$19,"Ambos")+SUMIFS('S8'!$I$6:$I$23,'S8'!$B$6:$B$23,$A110,'S8'!$E$6:$E$23,"Víctor")+SUMIFS('S8'!$I$6:$I$23,'S8'!$B$6:$B$23,$A110,'S8'!$E$6:$E$23,"Ambos")+SUMIFS('S9'!$I$6:$I$15,'S9'!$B$6:$B$15,$A110,'S9'!$E$6:$E$15,"Víctor")+SUMIFS('S9'!$I$6:$I$15,'S9'!$B$6:$B$15,$A110,'S9'!$E$6:$E$15,"Ambos")+SUMIFS('S10'!$I$6:$I$13,'S10'!$B$6:$B$13,$A110,'S10'!$E$6:$E$13,"Víctor")+SUMIFS('S10'!$I$6:$I$13,'S10'!$B$6:$B$13,$A110,'S10'!$E$6:$E$13,"Ambos")+SUMIFS('Holgura'!$I$6:$I$11,'Holgura'!$B$6:$B$11,$A110,'Holgura'!$E$6:$E$11,"Víctor")+SUMIFS('Holgura'!$I$6:$I$11,'Holgura'!$B$6:$B$11,$A110,'Holgura'!$E$6:$E$11,"Ambos")+SUMIFS('Entrega'!$I$6:$I$9,'Entrega'!$B$6:$B$9,$A110,'Entrega'!$E$6:$E$9,"Víctor")+SUMIFS('Entrega'!$I$6:$I$9,'Entrega'!$B$6:$B$9,$A110,'Entrega'!$E$6:$E$9,"Ambos")+SUMIFS('Defensa'!$I$6:$I$10,'Defensa'!$B$6:$B$10,$A110,'Defensa'!$E$6:$E$10,"Víctor")+SUMIFS('Defensa'!$I$6:$I$10,'Defensa'!$B$6:$B$10,$A110,'Defensa'!$E$6:$E$10,"Ambos")</f>
+        <f>SUMIFS('S1'!$I$6:$I$32,'S1'!$B$6:$B$32,$A110,'S1'!$E$6:$E$32,"Víctor")+SUMIFS('S1'!$I$6:$I$32,'S1'!$B$6:$B$32,$A110,'S1'!$E$6:$E$32,"Ambos")+SUMIFS('S2'!$I$6:$I$23,'S2'!$B$6:$B$23,$A110,'S2'!$E$6:$E$23,"Víctor")+SUMIFS('S2'!$I$6:$I$23,'S2'!$B$6:$B$23,$A110,'S2'!$E$6:$E$23,"Ambos")+SUMIFS('S3'!$I$6:$I$24,'S3'!$B$6:$B$24,$A110,'S3'!$E$6:$E$24,"Víctor")+SUMIFS('S3'!$I$6:$I$24,'S3'!$B$6:$B$24,$A110,'S3'!$E$6:$E$24,"Ambos")+SUMIFS('S4'!$I$6:$I$22,'S4'!$B$6:$B$22,$A110,'S4'!$E$6:$E$22,"Víctor")+SUMIFS('S4'!$I$6:$I$22,'S4'!$B$6:$B$22,$A110,'S4'!$E$6:$E$22,"Ambos")+SUMIFS('S5'!$I$6:$I$20,'S5'!$B$6:$B$20,$A110,'S5'!$E$6:$E$20,"Víctor")+SUMIFS('S5'!$I$6:$I$20,'S5'!$B$6:$B$20,$A110,'S5'!$E$6:$E$20,"Ambos")+SUMIFS('S6'!$I$6:$I$17,'S6'!$B$6:$B$17,$A110,'S6'!$E$6:$E$17,"Víctor")+SUMIFS('S6'!$I$6:$I$17,'S6'!$B$6:$B$17,$A110,'S6'!$E$6:$E$17,"Ambos")+SUMIFS('S7'!$I$6:$I$19,'S7'!$B$6:$B$19,$A110,'S7'!$E$6:$E$19,"Víctor")+SUMIFS('S7'!$I$6:$I$19,'S7'!$B$6:$B$19,$A110,'S7'!$E$6:$E$19,"Ambos")+SUMIFS('S8'!$I$6:$I$23,'S8'!$B$6:$B$23,$A110,'S8'!$E$6:$E$23,"Víctor")+SUMIFS('S8'!$I$6:$I$23,'S8'!$B$6:$B$23,$A110,'S8'!$E$6:$E$23,"Ambos")+SUMIFS('S9'!$I$6:$I$15,'S9'!$B$6:$B$15,$A110,'S9'!$E$6:$E$15,"Víctor")+SUMIFS('S9'!$I$6:$I$15,'S9'!$B$6:$B$15,$A110,'S9'!$E$6:$E$15,"Ambos")+SUMIFS('S10'!$I$6:$I$13,'S10'!$B$6:$B$13,$A110,'S10'!$E$6:$E$13,"Víctor")+SUMIFS('S10'!$I$6:$I$13,'S10'!$B$6:$B$13,$A110,'S10'!$E$6:$E$13,"Ambos")+SUMIFS('Holgura'!$I$6:$I$11,'Holgura'!$B$6:$B$11,$A110,'Holgura'!$E$6:$E$11,"Víctor")+SUMIFS('Holgura'!$I$6:$I$11,'Holgura'!$B$6:$B$11,$A110,'Holgura'!$E$6:$E$11,"Ambos")+SUMIFS('Entrega'!$I$6:$I$9,'Entrega'!$B$6:$B$9,$A110,'Entrega'!$E$6:$E$9,"Víctor")+SUMIFS('Entrega'!$I$6:$I$9,'Entrega'!$B$6:$B$9,$A110,'Entrega'!$E$6:$E$9,"Ambos")+SUMIFS('Defensa'!$I$6:$I$10,'Defensa'!$B$6:$B$10,$A110,'Defensa'!$E$6:$E$10,"Víctor")+SUMIFS('Defensa'!$I$6:$I$10,'Defensa'!$B$6:$B$10,$A110,'Defensa'!$E$6:$E$10,"Ambos")</f>
         <v/>
       </c>
       <c r="E110" s="21">
-        <f>SUMIFS('S1'!$I$6:$I$32,'S1'!$B$6:$B$32,$A110,'S1'!$E$6:$E$32,"Diego")+SUMIFS('S1'!$I$6:$I$32,'S1'!$B$6:$B$32,$A110,'S1'!$E$6:$E$32,"Ambos")+SUMIFS('S2'!$I$6:$I$23,'S2'!$B$6:$B$23,$A110,'S2'!$E$6:$E$23,"Diego")+SUMIFS('S2'!$I$6:$I$23,'S2'!$B$6:$B$23,$A110,'S2'!$E$6:$E$23,"Ambos")+SUMIFS('S3'!$I$6:$I$19,'S3'!$B$6:$B$19,$A110,'S3'!$E$6:$E$19,"Diego")+SUMIFS('S3'!$I$6:$I$19,'S3'!$B$6:$B$19,$A110,'S3'!$E$6:$E$19,"Ambos")+SUMIFS('S4'!$I$6:$I$20,'S4'!$B$6:$B$20,$A110,'S4'!$E$6:$E$20,"Diego")+SUMIFS('S4'!$I$6:$I$20,'S4'!$B$6:$B$20,$A110,'S4'!$E$6:$E$20,"Ambos")+SUMIFS('S5'!$I$6:$I$20,'S5'!$B$6:$B$20,$A110,'S5'!$E$6:$E$20,"Diego")+SUMIFS('S5'!$I$6:$I$20,'S5'!$B$6:$B$20,$A110,'S5'!$E$6:$E$20,"Ambos")+SUMIFS('S6'!$I$6:$I$17,'S6'!$B$6:$B$17,$A110,'S6'!$E$6:$E$17,"Diego")+SUMIFS('S6'!$I$6:$I$17,'S6'!$B$6:$B$17,$A110,'S6'!$E$6:$E$17,"Ambos")+SUMIFS('S7'!$I$6:$I$19,'S7'!$B$6:$B$19,$A110,'S7'!$E$6:$E$19,"Diego")+SUMIFS('S7'!$I$6:$I$19,'S7'!$B$6:$B$19,$A110,'S7'!$E$6:$E$19,"Ambos")+SUMIFS('S8'!$I$6:$I$23,'S8'!$B$6:$B$23,$A110,'S8'!$E$6:$E$23,"Diego")+SUMIFS('S8'!$I$6:$I$23,'S8'!$B$6:$B$23,$A110,'S8'!$E$6:$E$23,"Ambos")+SUMIFS('S9'!$I$6:$I$15,'S9'!$B$6:$B$15,$A110,'S9'!$E$6:$E$15,"Diego")+SUMIFS('S9'!$I$6:$I$15,'S9'!$B$6:$B$15,$A110,'S9'!$E$6:$E$15,"Ambos")+SUMIFS('S10'!$I$6:$I$13,'S10'!$B$6:$B$13,$A110,'S10'!$E$6:$E$13,"Diego")+SUMIFS('S10'!$I$6:$I$13,'S10'!$B$6:$B$13,$A110,'S10'!$E$6:$E$13,"Ambos")+SUMIFS('Holgura'!$I$6:$I$11,'Holgura'!$B$6:$B$11,$A110,'Holgura'!$E$6:$E$11,"Diego")+SUMIFS('Holgura'!$I$6:$I$11,'Holgura'!$B$6:$B$11,$A110,'Holgura'!$E$6:$E$11,"Ambos")+SUMIFS('Entrega'!$I$6:$I$9,'Entrega'!$B$6:$B$9,$A110,'Entrega'!$E$6:$E$9,"Diego")+SUMIFS('Entrega'!$I$6:$I$9,'Entrega'!$B$6:$B$9,$A110,'Entrega'!$E$6:$E$9,"Ambos")+SUMIFS('Defensa'!$I$6:$I$10,'Defensa'!$B$6:$B$10,$A110,'Defensa'!$E$6:$E$10,"Diego")+SUMIFS('Defensa'!$I$6:$I$10,'Defensa'!$B$6:$B$10,$A110,'Defensa'!$E$6:$E$10,"Ambos")</f>
+        <f>SUMIFS('S1'!$I$6:$I$32,'S1'!$B$6:$B$32,$A110,'S1'!$E$6:$E$32,"Diego")+SUMIFS('S1'!$I$6:$I$32,'S1'!$B$6:$B$32,$A110,'S1'!$E$6:$E$32,"Ambos")+SUMIFS('S2'!$I$6:$I$23,'S2'!$B$6:$B$23,$A110,'S2'!$E$6:$E$23,"Diego")+SUMIFS('S2'!$I$6:$I$23,'S2'!$B$6:$B$23,$A110,'S2'!$E$6:$E$23,"Ambos")+SUMIFS('S3'!$I$6:$I$24,'S3'!$B$6:$B$24,$A110,'S3'!$E$6:$E$24,"Diego")+SUMIFS('S3'!$I$6:$I$24,'S3'!$B$6:$B$24,$A110,'S3'!$E$6:$E$24,"Ambos")+SUMIFS('S4'!$I$6:$I$22,'S4'!$B$6:$B$22,$A110,'S4'!$E$6:$E$22,"Diego")+SUMIFS('S4'!$I$6:$I$22,'S4'!$B$6:$B$22,$A110,'S4'!$E$6:$E$22,"Ambos")+SUMIFS('S5'!$I$6:$I$20,'S5'!$B$6:$B$20,$A110,'S5'!$E$6:$E$20,"Diego")+SUMIFS('S5'!$I$6:$I$20,'S5'!$B$6:$B$20,$A110,'S5'!$E$6:$E$20,"Ambos")+SUMIFS('S6'!$I$6:$I$17,'S6'!$B$6:$B$17,$A110,'S6'!$E$6:$E$17,"Diego")+SUMIFS('S6'!$I$6:$I$17,'S6'!$B$6:$B$17,$A110,'S6'!$E$6:$E$17,"Ambos")+SUMIFS('S7'!$I$6:$I$19,'S7'!$B$6:$B$19,$A110,'S7'!$E$6:$E$19,"Diego")+SUMIFS('S7'!$I$6:$I$19,'S7'!$B$6:$B$19,$A110,'S7'!$E$6:$E$19,"Ambos")+SUMIFS('S8'!$I$6:$I$23,'S8'!$B$6:$B$23,$A110,'S8'!$E$6:$E$23,"Diego")+SUMIFS('S8'!$I$6:$I$23,'S8'!$B$6:$B$23,$A110,'S8'!$E$6:$E$23,"Ambos")+SUMIFS('S9'!$I$6:$I$15,'S9'!$B$6:$B$15,$A110,'S9'!$E$6:$E$15,"Diego")+SUMIFS('S9'!$I$6:$I$15,'S9'!$B$6:$B$15,$A110,'S9'!$E$6:$E$15,"Ambos")+SUMIFS('S10'!$I$6:$I$13,'S10'!$B$6:$B$13,$A110,'S10'!$E$6:$E$13,"Diego")+SUMIFS('S10'!$I$6:$I$13,'S10'!$B$6:$B$13,$A110,'S10'!$E$6:$E$13,"Ambos")+SUMIFS('Holgura'!$I$6:$I$11,'Holgura'!$B$6:$B$11,$A110,'Holgura'!$E$6:$E$11,"Diego")+SUMIFS('Holgura'!$I$6:$I$11,'Holgura'!$B$6:$B$11,$A110,'Holgura'!$E$6:$E$11,"Ambos")+SUMIFS('Entrega'!$I$6:$I$9,'Entrega'!$B$6:$B$9,$A110,'Entrega'!$E$6:$E$9,"Diego")+SUMIFS('Entrega'!$I$6:$I$9,'Entrega'!$B$6:$B$9,$A110,'Entrega'!$E$6:$E$9,"Ambos")+SUMIFS('Defensa'!$I$6:$I$10,'Defensa'!$B$6:$B$10,$A110,'Defensa'!$E$6:$E$10,"Diego")+SUMIFS('Defensa'!$I$6:$I$10,'Defensa'!$B$6:$B$10,$A110,'Defensa'!$E$6:$E$10,"Ambos")</f>
         <v/>
       </c>
       <c r="F110" s="21">
-        <f>COUNTIFS('S1'!$B$6:$B$32,$A110,'S1'!$E$6:$E$32,"Víctor")+COUNTIFS('S1'!$B$6:$B$32,$A110,'S1'!$E$6:$E$32,"Ambos")+COUNTIFS('S2'!$B$6:$B$23,$A110,'S2'!$E$6:$E$23,"Víctor")+COUNTIFS('S2'!$B$6:$B$23,$A110,'S2'!$E$6:$E$23,"Ambos")+COUNTIFS('S3'!$B$6:$B$19,$A110,'S3'!$E$6:$E$19,"Víctor")+COUNTIFS('S3'!$B$6:$B$19,$A110,'S3'!$E$6:$E$19,"Ambos")+COUNTIFS('S4'!$B$6:$B$20,$A110,'S4'!$E$6:$E$20,"Víctor")+COUNTIFS('S4'!$B$6:$B$20,$A110,'S4'!$E$6:$E$20,"Ambos")+COUNTIFS('S5'!$B$6:$B$20,$A110,'S5'!$E$6:$E$20,"Víctor")+COUNTIFS('S5'!$B$6:$B$20,$A110,'S5'!$E$6:$E$20,"Ambos")+COUNTIFS('S6'!$B$6:$B$17,$A110,'S6'!$E$6:$E$17,"Víctor")+COUNTIFS('S6'!$B$6:$B$17,$A110,'S6'!$E$6:$E$17,"Ambos")+COUNTIFS('S7'!$B$6:$B$19,$A110,'S7'!$E$6:$E$19,"Víctor")+COUNTIFS('S7'!$B$6:$B$19,$A110,'S7'!$E$6:$E$19,"Ambos")+COUNTIFS('S8'!$B$6:$B$23,$A110,'S8'!$E$6:$E$23,"Víctor")+COUNTIFS('S8'!$B$6:$B$23,$A110,'S8'!$E$6:$E$23,"Ambos")+COUNTIFS('S9'!$B$6:$B$15,$A110,'S9'!$E$6:$E$15,"Víctor")+COUNTIFS('S9'!$B$6:$B$15,$A110,'S9'!$E$6:$E$15,"Ambos")+COUNTIFS('S10'!$B$6:$B$13,$A110,'S10'!$E$6:$E$13,"Víctor")+COUNTIFS('S10'!$B$6:$B$13,$A110,'S10'!$E$6:$E$13,"Ambos")+COUNTIFS('Holgura'!$B$6:$B$11,$A110,'Holgura'!$E$6:$E$11,"Víctor")+COUNTIFS('Holgura'!$B$6:$B$11,$A110,'Holgura'!$E$6:$E$11,"Ambos")+COUNTIFS('Entrega'!$B$6:$B$9,$A110,'Entrega'!$E$6:$E$9,"Víctor")+COUNTIFS('Entrega'!$B$6:$B$9,$A110,'Entrega'!$E$6:$E$9,"Ambos")+COUNTIFS('Defensa'!$B$6:$B$10,$A110,'Defensa'!$E$6:$E$10,"Víctor")+COUNTIFS('Defensa'!$B$6:$B$10,$A110,'Defensa'!$E$6:$E$10,"Ambos")</f>
+        <f>COUNTIFS('S1'!$B$6:$B$32,$A110,'S1'!$E$6:$E$32,"Víctor")+COUNTIFS('S1'!$B$6:$B$32,$A110,'S1'!$E$6:$E$32,"Ambos")+COUNTIFS('S2'!$B$6:$B$23,$A110,'S2'!$E$6:$E$23,"Víctor")+COUNTIFS('S2'!$B$6:$B$23,$A110,'S2'!$E$6:$E$23,"Ambos")+COUNTIFS('S3'!$B$6:$B$24,$A110,'S3'!$E$6:$E$24,"Víctor")+COUNTIFS('S3'!$B$6:$B$24,$A110,'S3'!$E$6:$E$24,"Ambos")+COUNTIFS('S4'!$B$6:$B$22,$A110,'S4'!$E$6:$E$22,"Víctor")+COUNTIFS('S4'!$B$6:$B$22,$A110,'S4'!$E$6:$E$22,"Ambos")+COUNTIFS('S5'!$B$6:$B$20,$A110,'S5'!$E$6:$E$20,"Víctor")+COUNTIFS('S5'!$B$6:$B$20,$A110,'S5'!$E$6:$E$20,"Ambos")+COUNTIFS('S6'!$B$6:$B$17,$A110,'S6'!$E$6:$E$17,"Víctor")+COUNTIFS('S6'!$B$6:$B$17,$A110,'S6'!$E$6:$E$17,"Ambos")+COUNTIFS('S7'!$B$6:$B$19,$A110,'S7'!$E$6:$E$19,"Víctor")+COUNTIFS('S7'!$B$6:$B$19,$A110,'S7'!$E$6:$E$19,"Ambos")+COUNTIFS('S8'!$B$6:$B$23,$A110,'S8'!$E$6:$E$23,"Víctor")+COUNTIFS('S8'!$B$6:$B$23,$A110,'S8'!$E$6:$E$23,"Ambos")+COUNTIFS('S9'!$B$6:$B$15,$A110,'S9'!$E$6:$E$15,"Víctor")+COUNTIFS('S9'!$B$6:$B$15,$A110,'S9'!$E$6:$E$15,"Ambos")+COUNTIFS('S10'!$B$6:$B$13,$A110,'S10'!$E$6:$E$13,"Víctor")+COUNTIFS('S10'!$B$6:$B$13,$A110,'S10'!$E$6:$E$13,"Ambos")+COUNTIFS('Holgura'!$B$6:$B$11,$A110,'Holgura'!$E$6:$E$11,"Víctor")+COUNTIFS('Holgura'!$B$6:$B$11,$A110,'Holgura'!$E$6:$E$11,"Ambos")+COUNTIFS('Entrega'!$B$6:$B$9,$A110,'Entrega'!$E$6:$E$9,"Víctor")+COUNTIFS('Entrega'!$B$6:$B$9,$A110,'Entrega'!$E$6:$E$9,"Ambos")+COUNTIFS('Defensa'!$B$6:$B$10,$A110,'Defensa'!$E$6:$E$10,"Víctor")+COUNTIFS('Defensa'!$B$6:$B$10,$A110,'Defensa'!$E$6:$E$10,"Ambos")</f>
         <v/>
       </c>
       <c r="G110" s="21">
-        <f>COUNTIFS('S1'!$B$6:$B$32,$A110,'S1'!$E$6:$E$32,"Diego")+COUNTIFS('S1'!$B$6:$B$32,$A110,'S1'!$E$6:$E$32,"Ambos")+COUNTIFS('S2'!$B$6:$B$23,$A110,'S2'!$E$6:$E$23,"Diego")+COUNTIFS('S2'!$B$6:$B$23,$A110,'S2'!$E$6:$E$23,"Ambos")+COUNTIFS('S3'!$B$6:$B$19,$A110,'S3'!$E$6:$E$19,"Diego")+COUNTIFS('S3'!$B$6:$B$19,$A110,'S3'!$E$6:$E$19,"Ambos")+COUNTIFS('S4'!$B$6:$B$20,$A110,'S4'!$E$6:$E$20,"Diego")+COUNTIFS('S4'!$B$6:$B$20,$A110,'S4'!$E$6:$E$20,"Ambos")+COUNTIFS('S5'!$B$6:$B$20,$A110,'S5'!$E$6:$E$20,"Diego")+COUNTIFS('S5'!$B$6:$B$20,$A110,'S5'!$E$6:$E$20,"Ambos")+COUNTIFS('S6'!$B$6:$B$17,$A110,'S6'!$E$6:$E$17,"Diego")+COUNTIFS('S6'!$B$6:$B$17,$A110,'S6'!$E$6:$E$17,"Ambos")+COUNTIFS('S7'!$B$6:$B$19,$A110,'S7'!$E$6:$E$19,"Diego")+COUNTIFS('S7'!$B$6:$B$19,$A110,'S7'!$E$6:$E$19,"Ambos")+COUNTIFS('S8'!$B$6:$B$23,$A110,'S8'!$E$6:$E$23,"Diego")+COUNTIFS('S8'!$B$6:$B$23,$A110,'S8'!$E$6:$E$23,"Ambos")+COUNTIFS('S9'!$B$6:$B$15,$A110,'S9'!$E$6:$E$15,"Diego")+COUNTIFS('S9'!$B$6:$B$15,$A110,'S9'!$E$6:$E$15,"Ambos")+COUNTIFS('S10'!$B$6:$B$13,$A110,'S10'!$E$6:$E$13,"Diego")+COUNTIFS('S10'!$B$6:$B$13,$A110,'S10'!$E$6:$E$13,"Ambos")+COUNTIFS('Holgura'!$B$6:$B$11,$A110,'Holgura'!$E$6:$E$11,"Diego")+COUNTIFS('Holgura'!$B$6:$B$11,$A110,'Holgura'!$E$6:$E$11,"Ambos")+COUNTIFS('Entrega'!$B$6:$B$9,$A110,'Entrega'!$E$6:$E$9,"Diego")+COUNTIFS('Entrega'!$B$6:$B$9,$A110,'Entrega'!$E$6:$E$9,"Ambos")+COUNTIFS('Defensa'!$B$6:$B$10,$A110,'Defensa'!$E$6:$E$10,"Diego")+COUNTIFS('Defensa'!$B$6:$B$10,$A110,'Defensa'!$E$6:$E$10,"Ambos")</f>
+        <f>COUNTIFS('S1'!$B$6:$B$32,$A110,'S1'!$E$6:$E$32,"Diego")+COUNTIFS('S1'!$B$6:$B$32,$A110,'S1'!$E$6:$E$32,"Ambos")+COUNTIFS('S2'!$B$6:$B$23,$A110,'S2'!$E$6:$E$23,"Diego")+COUNTIFS('S2'!$B$6:$B$23,$A110,'S2'!$E$6:$E$23,"Ambos")+COUNTIFS('S3'!$B$6:$B$24,$A110,'S3'!$E$6:$E$24,"Diego")+COUNTIFS('S3'!$B$6:$B$24,$A110,'S3'!$E$6:$E$24,"Ambos")+COUNTIFS('S4'!$B$6:$B$22,$A110,'S4'!$E$6:$E$22,"Diego")+COUNTIFS('S4'!$B$6:$B$22,$A110,'S4'!$E$6:$E$22,"Ambos")+COUNTIFS('S5'!$B$6:$B$20,$A110,'S5'!$E$6:$E$20,"Diego")+COUNTIFS('S5'!$B$6:$B$20,$A110,'S5'!$E$6:$E$20,"Ambos")+COUNTIFS('S6'!$B$6:$B$17,$A110,'S6'!$E$6:$E$17,"Diego")+COUNTIFS('S6'!$B$6:$B$17,$A110,'S6'!$E$6:$E$17,"Ambos")+COUNTIFS('S7'!$B$6:$B$19,$A110,'S7'!$E$6:$E$19,"Diego")+COUNTIFS('S7'!$B$6:$B$19,$A110,'S7'!$E$6:$E$19,"Ambos")+COUNTIFS('S8'!$B$6:$B$23,$A110,'S8'!$E$6:$E$23,"Diego")+COUNTIFS('S8'!$B$6:$B$23,$A110,'S8'!$E$6:$E$23,"Ambos")+COUNTIFS('S9'!$B$6:$B$15,$A110,'S9'!$E$6:$E$15,"Diego")+COUNTIFS('S9'!$B$6:$B$15,$A110,'S9'!$E$6:$E$15,"Ambos")+COUNTIFS('S10'!$B$6:$B$13,$A110,'S10'!$E$6:$E$13,"Diego")+COUNTIFS('S10'!$B$6:$B$13,$A110,'S10'!$E$6:$E$13,"Ambos")+COUNTIFS('Holgura'!$B$6:$B$11,$A110,'Holgura'!$E$6:$E$11,"Diego")+COUNTIFS('Holgura'!$B$6:$B$11,$A110,'Holgura'!$E$6:$E$11,"Ambos")+COUNTIFS('Entrega'!$B$6:$B$9,$A110,'Entrega'!$E$6:$E$9,"Diego")+COUNTIFS('Entrega'!$B$6:$B$9,$A110,'Entrega'!$E$6:$E$9,"Ambos")+COUNTIFS('Defensa'!$B$6:$B$10,$A110,'Defensa'!$E$6:$E$10,"Diego")+COUNTIFS('Defensa'!$B$6:$B$10,$A110,'Defensa'!$E$6:$E$10,"Ambos")</f>
         <v/>
       </c>
     </row>
@@ -11754,19 +11775,19 @@
         <v/>
       </c>
       <c r="D111" s="21">
-        <f>SUMIFS('S1'!$I$6:$I$32,'S1'!$B$6:$B$32,$A111,'S1'!$E$6:$E$32,"Víctor")+SUMIFS('S1'!$I$6:$I$32,'S1'!$B$6:$B$32,$A111,'S1'!$E$6:$E$32,"Ambos")+SUMIFS('S2'!$I$6:$I$23,'S2'!$B$6:$B$23,$A111,'S2'!$E$6:$E$23,"Víctor")+SUMIFS('S2'!$I$6:$I$23,'S2'!$B$6:$B$23,$A111,'S2'!$E$6:$E$23,"Ambos")+SUMIFS('S3'!$I$6:$I$19,'S3'!$B$6:$B$19,$A111,'S3'!$E$6:$E$19,"Víctor")+SUMIFS('S3'!$I$6:$I$19,'S3'!$B$6:$B$19,$A111,'S3'!$E$6:$E$19,"Ambos")+SUMIFS('S4'!$I$6:$I$20,'S4'!$B$6:$B$20,$A111,'S4'!$E$6:$E$20,"Víctor")+SUMIFS('S4'!$I$6:$I$20,'S4'!$B$6:$B$20,$A111,'S4'!$E$6:$E$20,"Ambos")+SUMIFS('S5'!$I$6:$I$20,'S5'!$B$6:$B$20,$A111,'S5'!$E$6:$E$20,"Víctor")+SUMIFS('S5'!$I$6:$I$20,'S5'!$B$6:$B$20,$A111,'S5'!$E$6:$E$20,"Ambos")+SUMIFS('S6'!$I$6:$I$17,'S6'!$B$6:$B$17,$A111,'S6'!$E$6:$E$17,"Víctor")+SUMIFS('S6'!$I$6:$I$17,'S6'!$B$6:$B$17,$A111,'S6'!$E$6:$E$17,"Ambos")+SUMIFS('S7'!$I$6:$I$19,'S7'!$B$6:$B$19,$A111,'S7'!$E$6:$E$19,"Víctor")+SUMIFS('S7'!$I$6:$I$19,'S7'!$B$6:$B$19,$A111,'S7'!$E$6:$E$19,"Ambos")+SUMIFS('S8'!$I$6:$I$23,'S8'!$B$6:$B$23,$A111,'S8'!$E$6:$E$23,"Víctor")+SUMIFS('S8'!$I$6:$I$23,'S8'!$B$6:$B$23,$A111,'S8'!$E$6:$E$23,"Ambos")+SUMIFS('S9'!$I$6:$I$15,'S9'!$B$6:$B$15,$A111,'S9'!$E$6:$E$15,"Víctor")+SUMIFS('S9'!$I$6:$I$15,'S9'!$B$6:$B$15,$A111,'S9'!$E$6:$E$15,"Ambos")+SUMIFS('S10'!$I$6:$I$13,'S10'!$B$6:$B$13,$A111,'S10'!$E$6:$E$13,"Víctor")+SUMIFS('S10'!$I$6:$I$13,'S10'!$B$6:$B$13,$A111,'S10'!$E$6:$E$13,"Ambos")+SUMIFS('Holgura'!$I$6:$I$11,'Holgura'!$B$6:$B$11,$A111,'Holgura'!$E$6:$E$11,"Víctor")+SUMIFS('Holgura'!$I$6:$I$11,'Holgura'!$B$6:$B$11,$A111,'Holgura'!$E$6:$E$11,"Ambos")+SUMIFS('Entrega'!$I$6:$I$9,'Entrega'!$B$6:$B$9,$A111,'Entrega'!$E$6:$E$9,"Víctor")+SUMIFS('Entrega'!$I$6:$I$9,'Entrega'!$B$6:$B$9,$A111,'Entrega'!$E$6:$E$9,"Ambos")+SUMIFS('Defensa'!$I$6:$I$10,'Defensa'!$B$6:$B$10,$A111,'Defensa'!$E$6:$E$10,"Víctor")+SUMIFS('Defensa'!$I$6:$I$10,'Defensa'!$B$6:$B$10,$A111,'Defensa'!$E$6:$E$10,"Ambos")</f>
+        <f>SUMIFS('S1'!$I$6:$I$32,'S1'!$B$6:$B$32,$A111,'S1'!$E$6:$E$32,"Víctor")+SUMIFS('S1'!$I$6:$I$32,'S1'!$B$6:$B$32,$A111,'S1'!$E$6:$E$32,"Ambos")+SUMIFS('S2'!$I$6:$I$23,'S2'!$B$6:$B$23,$A111,'S2'!$E$6:$E$23,"Víctor")+SUMIFS('S2'!$I$6:$I$23,'S2'!$B$6:$B$23,$A111,'S2'!$E$6:$E$23,"Ambos")+SUMIFS('S3'!$I$6:$I$24,'S3'!$B$6:$B$24,$A111,'S3'!$E$6:$E$24,"Víctor")+SUMIFS('S3'!$I$6:$I$24,'S3'!$B$6:$B$24,$A111,'S3'!$E$6:$E$24,"Ambos")+SUMIFS('S4'!$I$6:$I$22,'S4'!$B$6:$B$22,$A111,'S4'!$E$6:$E$22,"Víctor")+SUMIFS('S4'!$I$6:$I$22,'S4'!$B$6:$B$22,$A111,'S4'!$E$6:$E$22,"Ambos")+SUMIFS('S5'!$I$6:$I$20,'S5'!$B$6:$B$20,$A111,'S5'!$E$6:$E$20,"Víctor")+SUMIFS('S5'!$I$6:$I$20,'S5'!$B$6:$B$20,$A111,'S5'!$E$6:$E$20,"Ambos")+SUMIFS('S6'!$I$6:$I$17,'S6'!$B$6:$B$17,$A111,'S6'!$E$6:$E$17,"Víctor")+SUMIFS('S6'!$I$6:$I$17,'S6'!$B$6:$B$17,$A111,'S6'!$E$6:$E$17,"Ambos")+SUMIFS('S7'!$I$6:$I$19,'S7'!$B$6:$B$19,$A111,'S7'!$E$6:$E$19,"Víctor")+SUMIFS('S7'!$I$6:$I$19,'S7'!$B$6:$B$19,$A111,'S7'!$E$6:$E$19,"Ambos")+SUMIFS('S8'!$I$6:$I$23,'S8'!$B$6:$B$23,$A111,'S8'!$E$6:$E$23,"Víctor")+SUMIFS('S8'!$I$6:$I$23,'S8'!$B$6:$B$23,$A111,'S8'!$E$6:$E$23,"Ambos")+SUMIFS('S9'!$I$6:$I$15,'S9'!$B$6:$B$15,$A111,'S9'!$E$6:$E$15,"Víctor")+SUMIFS('S9'!$I$6:$I$15,'S9'!$B$6:$B$15,$A111,'S9'!$E$6:$E$15,"Ambos")+SUMIFS('S10'!$I$6:$I$13,'S10'!$B$6:$B$13,$A111,'S10'!$E$6:$E$13,"Víctor")+SUMIFS('S10'!$I$6:$I$13,'S10'!$B$6:$B$13,$A111,'S10'!$E$6:$E$13,"Ambos")+SUMIFS('Holgura'!$I$6:$I$11,'Holgura'!$B$6:$B$11,$A111,'Holgura'!$E$6:$E$11,"Víctor")+SUMIFS('Holgura'!$I$6:$I$11,'Holgura'!$B$6:$B$11,$A111,'Holgura'!$E$6:$E$11,"Ambos")+SUMIFS('Entrega'!$I$6:$I$9,'Entrega'!$B$6:$B$9,$A111,'Entrega'!$E$6:$E$9,"Víctor")+SUMIFS('Entrega'!$I$6:$I$9,'Entrega'!$B$6:$B$9,$A111,'Entrega'!$E$6:$E$9,"Ambos")+SUMIFS('Defensa'!$I$6:$I$10,'Defensa'!$B$6:$B$10,$A111,'Defensa'!$E$6:$E$10,"Víctor")+SUMIFS('Defensa'!$I$6:$I$10,'Defensa'!$B$6:$B$10,$A111,'Defensa'!$E$6:$E$10,"Ambos")</f>
         <v/>
       </c>
       <c r="E111" s="21">
-        <f>SUMIFS('S1'!$I$6:$I$32,'S1'!$B$6:$B$32,$A111,'S1'!$E$6:$E$32,"Diego")+SUMIFS('S1'!$I$6:$I$32,'S1'!$B$6:$B$32,$A111,'S1'!$E$6:$E$32,"Ambos")+SUMIFS('S2'!$I$6:$I$23,'S2'!$B$6:$B$23,$A111,'S2'!$E$6:$E$23,"Diego")+SUMIFS('S2'!$I$6:$I$23,'S2'!$B$6:$B$23,$A111,'S2'!$E$6:$E$23,"Ambos")+SUMIFS('S3'!$I$6:$I$19,'S3'!$B$6:$B$19,$A111,'S3'!$E$6:$E$19,"Diego")+SUMIFS('S3'!$I$6:$I$19,'S3'!$B$6:$B$19,$A111,'S3'!$E$6:$E$19,"Ambos")+SUMIFS('S4'!$I$6:$I$20,'S4'!$B$6:$B$20,$A111,'S4'!$E$6:$E$20,"Diego")+SUMIFS('S4'!$I$6:$I$20,'S4'!$B$6:$B$20,$A111,'S4'!$E$6:$E$20,"Ambos")+SUMIFS('S5'!$I$6:$I$20,'S5'!$B$6:$B$20,$A111,'S5'!$E$6:$E$20,"Diego")+SUMIFS('S5'!$I$6:$I$20,'S5'!$B$6:$B$20,$A111,'S5'!$E$6:$E$20,"Ambos")+SUMIFS('S6'!$I$6:$I$17,'S6'!$B$6:$B$17,$A111,'S6'!$E$6:$E$17,"Diego")+SUMIFS('S6'!$I$6:$I$17,'S6'!$B$6:$B$17,$A111,'S6'!$E$6:$E$17,"Ambos")+SUMIFS('S7'!$I$6:$I$19,'S7'!$B$6:$B$19,$A111,'S7'!$E$6:$E$19,"Diego")+SUMIFS('S7'!$I$6:$I$19,'S7'!$B$6:$B$19,$A111,'S7'!$E$6:$E$19,"Ambos")+SUMIFS('S8'!$I$6:$I$23,'S8'!$B$6:$B$23,$A111,'S8'!$E$6:$E$23,"Diego")+SUMIFS('S8'!$I$6:$I$23,'S8'!$B$6:$B$23,$A111,'S8'!$E$6:$E$23,"Ambos")+SUMIFS('S9'!$I$6:$I$15,'S9'!$B$6:$B$15,$A111,'S9'!$E$6:$E$15,"Diego")+SUMIFS('S9'!$I$6:$I$15,'S9'!$B$6:$B$15,$A111,'S9'!$E$6:$E$15,"Ambos")+SUMIFS('S10'!$I$6:$I$13,'S10'!$B$6:$B$13,$A111,'S10'!$E$6:$E$13,"Diego")+SUMIFS('S10'!$I$6:$I$13,'S10'!$B$6:$B$13,$A111,'S10'!$E$6:$E$13,"Ambos")+SUMIFS('Holgura'!$I$6:$I$11,'Holgura'!$B$6:$B$11,$A111,'Holgura'!$E$6:$E$11,"Diego")+SUMIFS('Holgura'!$I$6:$I$11,'Holgura'!$B$6:$B$11,$A111,'Holgura'!$E$6:$E$11,"Ambos")+SUMIFS('Entrega'!$I$6:$I$9,'Entrega'!$B$6:$B$9,$A111,'Entrega'!$E$6:$E$9,"Diego")+SUMIFS('Entrega'!$I$6:$I$9,'Entrega'!$B$6:$B$9,$A111,'Entrega'!$E$6:$E$9,"Ambos")+SUMIFS('Defensa'!$I$6:$I$10,'Defensa'!$B$6:$B$10,$A111,'Defensa'!$E$6:$E$10,"Diego")+SUMIFS('Defensa'!$I$6:$I$10,'Defensa'!$B$6:$B$10,$A111,'Defensa'!$E$6:$E$10,"Ambos")</f>
+        <f>SUMIFS('S1'!$I$6:$I$32,'S1'!$B$6:$B$32,$A111,'S1'!$E$6:$E$32,"Diego")+SUMIFS('S1'!$I$6:$I$32,'S1'!$B$6:$B$32,$A111,'S1'!$E$6:$E$32,"Ambos")+SUMIFS('S2'!$I$6:$I$23,'S2'!$B$6:$B$23,$A111,'S2'!$E$6:$E$23,"Diego")+SUMIFS('S2'!$I$6:$I$23,'S2'!$B$6:$B$23,$A111,'S2'!$E$6:$E$23,"Ambos")+SUMIFS('S3'!$I$6:$I$24,'S3'!$B$6:$B$24,$A111,'S3'!$E$6:$E$24,"Diego")+SUMIFS('S3'!$I$6:$I$24,'S3'!$B$6:$B$24,$A111,'S3'!$E$6:$E$24,"Ambos")+SUMIFS('S4'!$I$6:$I$22,'S4'!$B$6:$B$22,$A111,'S4'!$E$6:$E$22,"Diego")+SUMIFS('S4'!$I$6:$I$22,'S4'!$B$6:$B$22,$A111,'S4'!$E$6:$E$22,"Ambos")+SUMIFS('S5'!$I$6:$I$20,'S5'!$B$6:$B$20,$A111,'S5'!$E$6:$E$20,"Diego")+SUMIFS('S5'!$I$6:$I$20,'S5'!$B$6:$B$20,$A111,'S5'!$E$6:$E$20,"Ambos")+SUMIFS('S6'!$I$6:$I$17,'S6'!$B$6:$B$17,$A111,'S6'!$E$6:$E$17,"Diego")+SUMIFS('S6'!$I$6:$I$17,'S6'!$B$6:$B$17,$A111,'S6'!$E$6:$E$17,"Ambos")+SUMIFS('S7'!$I$6:$I$19,'S7'!$B$6:$B$19,$A111,'S7'!$E$6:$E$19,"Diego")+SUMIFS('S7'!$I$6:$I$19,'S7'!$B$6:$B$19,$A111,'S7'!$E$6:$E$19,"Ambos")+SUMIFS('S8'!$I$6:$I$23,'S8'!$B$6:$B$23,$A111,'S8'!$E$6:$E$23,"Diego")+SUMIFS('S8'!$I$6:$I$23,'S8'!$B$6:$B$23,$A111,'S8'!$E$6:$E$23,"Ambos")+SUMIFS('S9'!$I$6:$I$15,'S9'!$B$6:$B$15,$A111,'S9'!$E$6:$E$15,"Diego")+SUMIFS('S9'!$I$6:$I$15,'S9'!$B$6:$B$15,$A111,'S9'!$E$6:$E$15,"Ambos")+SUMIFS('S10'!$I$6:$I$13,'S10'!$B$6:$B$13,$A111,'S10'!$E$6:$E$13,"Diego")+SUMIFS('S10'!$I$6:$I$13,'S10'!$B$6:$B$13,$A111,'S10'!$E$6:$E$13,"Ambos")+SUMIFS('Holgura'!$I$6:$I$11,'Holgura'!$B$6:$B$11,$A111,'Holgura'!$E$6:$E$11,"Diego")+SUMIFS('Holgura'!$I$6:$I$11,'Holgura'!$B$6:$B$11,$A111,'Holgura'!$E$6:$E$11,"Ambos")+SUMIFS('Entrega'!$I$6:$I$9,'Entrega'!$B$6:$B$9,$A111,'Entrega'!$E$6:$E$9,"Diego")+SUMIFS('Entrega'!$I$6:$I$9,'Entrega'!$B$6:$B$9,$A111,'Entrega'!$E$6:$E$9,"Ambos")+SUMIFS('Defensa'!$I$6:$I$10,'Defensa'!$B$6:$B$10,$A111,'Defensa'!$E$6:$E$10,"Diego")+SUMIFS('Defensa'!$I$6:$I$10,'Defensa'!$B$6:$B$10,$A111,'Defensa'!$E$6:$E$10,"Ambos")</f>
         <v/>
       </c>
       <c r="F111" s="21">
-        <f>COUNTIFS('S1'!$B$6:$B$32,$A111,'S1'!$E$6:$E$32,"Víctor")+COUNTIFS('S1'!$B$6:$B$32,$A111,'S1'!$E$6:$E$32,"Ambos")+COUNTIFS('S2'!$B$6:$B$23,$A111,'S2'!$E$6:$E$23,"Víctor")+COUNTIFS('S2'!$B$6:$B$23,$A111,'S2'!$E$6:$E$23,"Ambos")+COUNTIFS('S3'!$B$6:$B$19,$A111,'S3'!$E$6:$E$19,"Víctor")+COUNTIFS('S3'!$B$6:$B$19,$A111,'S3'!$E$6:$E$19,"Ambos")+COUNTIFS('S4'!$B$6:$B$20,$A111,'S4'!$E$6:$E$20,"Víctor")+COUNTIFS('S4'!$B$6:$B$20,$A111,'S4'!$E$6:$E$20,"Ambos")+COUNTIFS('S5'!$B$6:$B$20,$A111,'S5'!$E$6:$E$20,"Víctor")+COUNTIFS('S5'!$B$6:$B$20,$A111,'S5'!$E$6:$E$20,"Ambos")+COUNTIFS('S6'!$B$6:$B$17,$A111,'S6'!$E$6:$E$17,"Víctor")+COUNTIFS('S6'!$B$6:$B$17,$A111,'S6'!$E$6:$E$17,"Ambos")+COUNTIFS('S7'!$B$6:$B$19,$A111,'S7'!$E$6:$E$19,"Víctor")+COUNTIFS('S7'!$B$6:$B$19,$A111,'S7'!$E$6:$E$19,"Ambos")+COUNTIFS('S8'!$B$6:$B$23,$A111,'S8'!$E$6:$E$23,"Víctor")+COUNTIFS('S8'!$B$6:$B$23,$A111,'S8'!$E$6:$E$23,"Ambos")+COUNTIFS('S9'!$B$6:$B$15,$A111,'S9'!$E$6:$E$15,"Víctor")+COUNTIFS('S9'!$B$6:$B$15,$A111,'S9'!$E$6:$E$15,"Ambos")+COUNTIFS('S10'!$B$6:$B$13,$A111,'S10'!$E$6:$E$13,"Víctor")+COUNTIFS('S10'!$B$6:$B$13,$A111,'S10'!$E$6:$E$13,"Ambos")+COUNTIFS('Holgura'!$B$6:$B$11,$A111,'Holgura'!$E$6:$E$11,"Víctor")+COUNTIFS('Holgura'!$B$6:$B$11,$A111,'Holgura'!$E$6:$E$11,"Ambos")+COUNTIFS('Entrega'!$B$6:$B$9,$A111,'Entrega'!$E$6:$E$9,"Víctor")+COUNTIFS('Entrega'!$B$6:$B$9,$A111,'Entrega'!$E$6:$E$9,"Ambos")+COUNTIFS('Defensa'!$B$6:$B$10,$A111,'Defensa'!$E$6:$E$10,"Víctor")+COUNTIFS('Defensa'!$B$6:$B$10,$A111,'Defensa'!$E$6:$E$10,"Ambos")</f>
+        <f>COUNTIFS('S1'!$B$6:$B$32,$A111,'S1'!$E$6:$E$32,"Víctor")+COUNTIFS('S1'!$B$6:$B$32,$A111,'S1'!$E$6:$E$32,"Ambos")+COUNTIFS('S2'!$B$6:$B$23,$A111,'S2'!$E$6:$E$23,"Víctor")+COUNTIFS('S2'!$B$6:$B$23,$A111,'S2'!$E$6:$E$23,"Ambos")+COUNTIFS('S3'!$B$6:$B$24,$A111,'S3'!$E$6:$E$24,"Víctor")+COUNTIFS('S3'!$B$6:$B$24,$A111,'S3'!$E$6:$E$24,"Ambos")+COUNTIFS('S4'!$B$6:$B$22,$A111,'S4'!$E$6:$E$22,"Víctor")+COUNTIFS('S4'!$B$6:$B$22,$A111,'S4'!$E$6:$E$22,"Ambos")+COUNTIFS('S5'!$B$6:$B$20,$A111,'S5'!$E$6:$E$20,"Víctor")+COUNTIFS('S5'!$B$6:$B$20,$A111,'S5'!$E$6:$E$20,"Ambos")+COUNTIFS('S6'!$B$6:$B$17,$A111,'S6'!$E$6:$E$17,"Víctor")+COUNTIFS('S6'!$B$6:$B$17,$A111,'S6'!$E$6:$E$17,"Ambos")+COUNTIFS('S7'!$B$6:$B$19,$A111,'S7'!$E$6:$E$19,"Víctor")+COUNTIFS('S7'!$B$6:$B$19,$A111,'S7'!$E$6:$E$19,"Ambos")+COUNTIFS('S8'!$B$6:$B$23,$A111,'S8'!$E$6:$E$23,"Víctor")+COUNTIFS('S8'!$B$6:$B$23,$A111,'S8'!$E$6:$E$23,"Ambos")+COUNTIFS('S9'!$B$6:$B$15,$A111,'S9'!$E$6:$E$15,"Víctor")+COUNTIFS('S9'!$B$6:$B$15,$A111,'S9'!$E$6:$E$15,"Ambos")+COUNTIFS('S10'!$B$6:$B$13,$A111,'S10'!$E$6:$E$13,"Víctor")+COUNTIFS('S10'!$B$6:$B$13,$A111,'S10'!$E$6:$E$13,"Ambos")+COUNTIFS('Holgura'!$B$6:$B$11,$A111,'Holgura'!$E$6:$E$11,"Víctor")+COUNTIFS('Holgura'!$B$6:$B$11,$A111,'Holgura'!$E$6:$E$11,"Ambos")+COUNTIFS('Entrega'!$B$6:$B$9,$A111,'Entrega'!$E$6:$E$9,"Víctor")+COUNTIFS('Entrega'!$B$6:$B$9,$A111,'Entrega'!$E$6:$E$9,"Ambos")+COUNTIFS('Defensa'!$B$6:$B$10,$A111,'Defensa'!$E$6:$E$10,"Víctor")+COUNTIFS('Defensa'!$B$6:$B$10,$A111,'Defensa'!$E$6:$E$10,"Ambos")</f>
         <v/>
       </c>
       <c r="G111" s="21">
-        <f>COUNTIFS('S1'!$B$6:$B$32,$A111,'S1'!$E$6:$E$32,"Diego")+COUNTIFS('S1'!$B$6:$B$32,$A111,'S1'!$E$6:$E$32,"Ambos")+COUNTIFS('S2'!$B$6:$B$23,$A111,'S2'!$E$6:$E$23,"Diego")+COUNTIFS('S2'!$B$6:$B$23,$A111,'S2'!$E$6:$E$23,"Ambos")+COUNTIFS('S3'!$B$6:$B$19,$A111,'S3'!$E$6:$E$19,"Diego")+COUNTIFS('S3'!$B$6:$B$19,$A111,'S3'!$E$6:$E$19,"Ambos")+COUNTIFS('S4'!$B$6:$B$20,$A111,'S4'!$E$6:$E$20,"Diego")+COUNTIFS('S4'!$B$6:$B$20,$A111,'S4'!$E$6:$E$20,"Ambos")+COUNTIFS('S5'!$B$6:$B$20,$A111,'S5'!$E$6:$E$20,"Diego")+COUNTIFS('S5'!$B$6:$B$20,$A111,'S5'!$E$6:$E$20,"Ambos")+COUNTIFS('S6'!$B$6:$B$17,$A111,'S6'!$E$6:$E$17,"Diego")+COUNTIFS('S6'!$B$6:$B$17,$A111,'S6'!$E$6:$E$17,"Ambos")+COUNTIFS('S7'!$B$6:$B$19,$A111,'S7'!$E$6:$E$19,"Diego")+COUNTIFS('S7'!$B$6:$B$19,$A111,'S7'!$E$6:$E$19,"Ambos")+COUNTIFS('S8'!$B$6:$B$23,$A111,'S8'!$E$6:$E$23,"Diego")+COUNTIFS('S8'!$B$6:$B$23,$A111,'S8'!$E$6:$E$23,"Ambos")+COUNTIFS('S9'!$B$6:$B$15,$A111,'S9'!$E$6:$E$15,"Diego")+COUNTIFS('S9'!$B$6:$B$15,$A111,'S9'!$E$6:$E$15,"Ambos")+COUNTIFS('S10'!$B$6:$B$13,$A111,'S10'!$E$6:$E$13,"Diego")+COUNTIFS('S10'!$B$6:$B$13,$A111,'S10'!$E$6:$E$13,"Ambos")+COUNTIFS('Holgura'!$B$6:$B$11,$A111,'Holgura'!$E$6:$E$11,"Diego")+COUNTIFS('Holgura'!$B$6:$B$11,$A111,'Holgura'!$E$6:$E$11,"Ambos")+COUNTIFS('Entrega'!$B$6:$B$9,$A111,'Entrega'!$E$6:$E$9,"Diego")+COUNTIFS('Entrega'!$B$6:$B$9,$A111,'Entrega'!$E$6:$E$9,"Ambos")+COUNTIFS('Defensa'!$B$6:$B$10,$A111,'Defensa'!$E$6:$E$10,"Diego")+COUNTIFS('Defensa'!$B$6:$B$10,$A111,'Defensa'!$E$6:$E$10,"Ambos")</f>
+        <f>COUNTIFS('S1'!$B$6:$B$32,$A111,'S1'!$E$6:$E$32,"Diego")+COUNTIFS('S1'!$B$6:$B$32,$A111,'S1'!$E$6:$E$32,"Ambos")+COUNTIFS('S2'!$B$6:$B$23,$A111,'S2'!$E$6:$E$23,"Diego")+COUNTIFS('S2'!$B$6:$B$23,$A111,'S2'!$E$6:$E$23,"Ambos")+COUNTIFS('S3'!$B$6:$B$24,$A111,'S3'!$E$6:$E$24,"Diego")+COUNTIFS('S3'!$B$6:$B$24,$A111,'S3'!$E$6:$E$24,"Ambos")+COUNTIFS('S4'!$B$6:$B$22,$A111,'S4'!$E$6:$E$22,"Diego")+COUNTIFS('S4'!$B$6:$B$22,$A111,'S4'!$E$6:$E$22,"Ambos")+COUNTIFS('S5'!$B$6:$B$20,$A111,'S5'!$E$6:$E$20,"Diego")+COUNTIFS('S5'!$B$6:$B$20,$A111,'S5'!$E$6:$E$20,"Ambos")+COUNTIFS('S6'!$B$6:$B$17,$A111,'S6'!$E$6:$E$17,"Diego")+COUNTIFS('S6'!$B$6:$B$17,$A111,'S6'!$E$6:$E$17,"Ambos")+COUNTIFS('S7'!$B$6:$B$19,$A111,'S7'!$E$6:$E$19,"Diego")+COUNTIFS('S7'!$B$6:$B$19,$A111,'S7'!$E$6:$E$19,"Ambos")+COUNTIFS('S8'!$B$6:$B$23,$A111,'S8'!$E$6:$E$23,"Diego")+COUNTIFS('S8'!$B$6:$B$23,$A111,'S8'!$E$6:$E$23,"Ambos")+COUNTIFS('S9'!$B$6:$B$15,$A111,'S9'!$E$6:$E$15,"Diego")+COUNTIFS('S9'!$B$6:$B$15,$A111,'S9'!$E$6:$E$15,"Ambos")+COUNTIFS('S10'!$B$6:$B$13,$A111,'S10'!$E$6:$E$13,"Diego")+COUNTIFS('S10'!$B$6:$B$13,$A111,'S10'!$E$6:$E$13,"Ambos")+COUNTIFS('Holgura'!$B$6:$B$11,$A111,'Holgura'!$E$6:$E$11,"Diego")+COUNTIFS('Holgura'!$B$6:$B$11,$A111,'Holgura'!$E$6:$E$11,"Ambos")+COUNTIFS('Entrega'!$B$6:$B$9,$A111,'Entrega'!$E$6:$E$9,"Diego")+COUNTIFS('Entrega'!$B$6:$B$9,$A111,'Entrega'!$E$6:$E$9,"Ambos")+COUNTIFS('Defensa'!$B$6:$B$10,$A111,'Defensa'!$E$6:$E$10,"Diego")+COUNTIFS('Defensa'!$B$6:$B$10,$A111,'Defensa'!$E$6:$E$10,"Ambos")</f>
         <v/>
       </c>
     </row>
@@ -11783,19 +11804,19 @@
         <v/>
       </c>
       <c r="D112" s="21">
-        <f>SUMIFS('S1'!$I$6:$I$32,'S1'!$B$6:$B$32,$A112,'S1'!$E$6:$E$32,"Víctor")+SUMIFS('S1'!$I$6:$I$32,'S1'!$B$6:$B$32,$A112,'S1'!$E$6:$E$32,"Ambos")+SUMIFS('S2'!$I$6:$I$23,'S2'!$B$6:$B$23,$A112,'S2'!$E$6:$E$23,"Víctor")+SUMIFS('S2'!$I$6:$I$23,'S2'!$B$6:$B$23,$A112,'S2'!$E$6:$E$23,"Ambos")+SUMIFS('S3'!$I$6:$I$19,'S3'!$B$6:$B$19,$A112,'S3'!$E$6:$E$19,"Víctor")+SUMIFS('S3'!$I$6:$I$19,'S3'!$B$6:$B$19,$A112,'S3'!$E$6:$E$19,"Ambos")+SUMIFS('S4'!$I$6:$I$20,'S4'!$B$6:$B$20,$A112,'S4'!$E$6:$E$20,"Víctor")+SUMIFS('S4'!$I$6:$I$20,'S4'!$B$6:$B$20,$A112,'S4'!$E$6:$E$20,"Ambos")+SUMIFS('S5'!$I$6:$I$20,'S5'!$B$6:$B$20,$A112,'S5'!$E$6:$E$20,"Víctor")+SUMIFS('S5'!$I$6:$I$20,'S5'!$B$6:$B$20,$A112,'S5'!$E$6:$E$20,"Ambos")+SUMIFS('S6'!$I$6:$I$17,'S6'!$B$6:$B$17,$A112,'S6'!$E$6:$E$17,"Víctor")+SUMIFS('S6'!$I$6:$I$17,'S6'!$B$6:$B$17,$A112,'S6'!$E$6:$E$17,"Ambos")+SUMIFS('S7'!$I$6:$I$19,'S7'!$B$6:$B$19,$A112,'S7'!$E$6:$E$19,"Víctor")+SUMIFS('S7'!$I$6:$I$19,'S7'!$B$6:$B$19,$A112,'S7'!$E$6:$E$19,"Ambos")+SUMIFS('S8'!$I$6:$I$23,'S8'!$B$6:$B$23,$A112,'S8'!$E$6:$E$23,"Víctor")+SUMIFS('S8'!$I$6:$I$23,'S8'!$B$6:$B$23,$A112,'S8'!$E$6:$E$23,"Ambos")+SUMIFS('S9'!$I$6:$I$15,'S9'!$B$6:$B$15,$A112,'S9'!$E$6:$E$15,"Víctor")+SUMIFS('S9'!$I$6:$I$15,'S9'!$B$6:$B$15,$A112,'S9'!$E$6:$E$15,"Ambos")+SUMIFS('S10'!$I$6:$I$13,'S10'!$B$6:$B$13,$A112,'S10'!$E$6:$E$13,"Víctor")+SUMIFS('S10'!$I$6:$I$13,'S10'!$B$6:$B$13,$A112,'S10'!$E$6:$E$13,"Ambos")+SUMIFS('Holgura'!$I$6:$I$11,'Holgura'!$B$6:$B$11,$A112,'Holgura'!$E$6:$E$11,"Víctor")+SUMIFS('Holgura'!$I$6:$I$11,'Holgura'!$B$6:$B$11,$A112,'Holgura'!$E$6:$E$11,"Ambos")+SUMIFS('Entrega'!$I$6:$I$9,'Entrega'!$B$6:$B$9,$A112,'Entrega'!$E$6:$E$9,"Víctor")+SUMIFS('Entrega'!$I$6:$I$9,'Entrega'!$B$6:$B$9,$A112,'Entrega'!$E$6:$E$9,"Ambos")+SUMIFS('Defensa'!$I$6:$I$10,'Defensa'!$B$6:$B$10,$A112,'Defensa'!$E$6:$E$10,"Víctor")+SUMIFS('Defensa'!$I$6:$I$10,'Defensa'!$B$6:$B$10,$A112,'Defensa'!$E$6:$E$10,"Ambos")</f>
+        <f>SUMIFS('S1'!$I$6:$I$32,'S1'!$B$6:$B$32,$A112,'S1'!$E$6:$E$32,"Víctor")+SUMIFS('S1'!$I$6:$I$32,'S1'!$B$6:$B$32,$A112,'S1'!$E$6:$E$32,"Ambos")+SUMIFS('S2'!$I$6:$I$23,'S2'!$B$6:$B$23,$A112,'S2'!$E$6:$E$23,"Víctor")+SUMIFS('S2'!$I$6:$I$23,'S2'!$B$6:$B$23,$A112,'S2'!$E$6:$E$23,"Ambos")+SUMIFS('S3'!$I$6:$I$24,'S3'!$B$6:$B$24,$A112,'S3'!$E$6:$E$24,"Víctor")+SUMIFS('S3'!$I$6:$I$24,'S3'!$B$6:$B$24,$A112,'S3'!$E$6:$E$24,"Ambos")+SUMIFS('S4'!$I$6:$I$22,'S4'!$B$6:$B$22,$A112,'S4'!$E$6:$E$22,"Víctor")+SUMIFS('S4'!$I$6:$I$22,'S4'!$B$6:$B$22,$A112,'S4'!$E$6:$E$22,"Ambos")+SUMIFS('S5'!$I$6:$I$20,'S5'!$B$6:$B$20,$A112,'S5'!$E$6:$E$20,"Víctor")+SUMIFS('S5'!$I$6:$I$20,'S5'!$B$6:$B$20,$A112,'S5'!$E$6:$E$20,"Ambos")+SUMIFS('S6'!$I$6:$I$17,'S6'!$B$6:$B$17,$A112,'S6'!$E$6:$E$17,"Víctor")+SUMIFS('S6'!$I$6:$I$17,'S6'!$B$6:$B$17,$A112,'S6'!$E$6:$E$17,"Ambos")+SUMIFS('S7'!$I$6:$I$19,'S7'!$B$6:$B$19,$A112,'S7'!$E$6:$E$19,"Víctor")+SUMIFS('S7'!$I$6:$I$19,'S7'!$B$6:$B$19,$A112,'S7'!$E$6:$E$19,"Ambos")+SUMIFS('S8'!$I$6:$I$23,'S8'!$B$6:$B$23,$A112,'S8'!$E$6:$E$23,"Víctor")+SUMIFS('S8'!$I$6:$I$23,'S8'!$B$6:$B$23,$A112,'S8'!$E$6:$E$23,"Ambos")+SUMIFS('S9'!$I$6:$I$15,'S9'!$B$6:$B$15,$A112,'S9'!$E$6:$E$15,"Víctor")+SUMIFS('S9'!$I$6:$I$15,'S9'!$B$6:$B$15,$A112,'S9'!$E$6:$E$15,"Ambos")+SUMIFS('S10'!$I$6:$I$13,'S10'!$B$6:$B$13,$A112,'S10'!$E$6:$E$13,"Víctor")+SUMIFS('S10'!$I$6:$I$13,'S10'!$B$6:$B$13,$A112,'S10'!$E$6:$E$13,"Ambos")+SUMIFS('Holgura'!$I$6:$I$11,'Holgura'!$B$6:$B$11,$A112,'Holgura'!$E$6:$E$11,"Víctor")+SUMIFS('Holgura'!$I$6:$I$11,'Holgura'!$B$6:$B$11,$A112,'Holgura'!$E$6:$E$11,"Ambos")+SUMIFS('Entrega'!$I$6:$I$9,'Entrega'!$B$6:$B$9,$A112,'Entrega'!$E$6:$E$9,"Víctor")+SUMIFS('Entrega'!$I$6:$I$9,'Entrega'!$B$6:$B$9,$A112,'Entrega'!$E$6:$E$9,"Ambos")+SUMIFS('Defensa'!$I$6:$I$10,'Defensa'!$B$6:$B$10,$A112,'Defensa'!$E$6:$E$10,"Víctor")+SUMIFS('Defensa'!$I$6:$I$10,'Defensa'!$B$6:$B$10,$A112,'Defensa'!$E$6:$E$10,"Ambos")</f>
         <v/>
       </c>
       <c r="E112" s="21">
-        <f>SUMIFS('S1'!$I$6:$I$32,'S1'!$B$6:$B$32,$A112,'S1'!$E$6:$E$32,"Diego")+SUMIFS('S1'!$I$6:$I$32,'S1'!$B$6:$B$32,$A112,'S1'!$E$6:$E$32,"Ambos")+SUMIFS('S2'!$I$6:$I$23,'S2'!$B$6:$B$23,$A112,'S2'!$E$6:$E$23,"Diego")+SUMIFS('S2'!$I$6:$I$23,'S2'!$B$6:$B$23,$A112,'S2'!$E$6:$E$23,"Ambos")+SUMIFS('S3'!$I$6:$I$19,'S3'!$B$6:$B$19,$A112,'S3'!$E$6:$E$19,"Diego")+SUMIFS('S3'!$I$6:$I$19,'S3'!$B$6:$B$19,$A112,'S3'!$E$6:$E$19,"Ambos")+SUMIFS('S4'!$I$6:$I$20,'S4'!$B$6:$B$20,$A112,'S4'!$E$6:$E$20,"Diego")+SUMIFS('S4'!$I$6:$I$20,'S4'!$B$6:$B$20,$A112,'S4'!$E$6:$E$20,"Ambos")+SUMIFS('S5'!$I$6:$I$20,'S5'!$B$6:$B$20,$A112,'S5'!$E$6:$E$20,"Diego")+SUMIFS('S5'!$I$6:$I$20,'S5'!$B$6:$B$20,$A112,'S5'!$E$6:$E$20,"Ambos")+SUMIFS('S6'!$I$6:$I$17,'S6'!$B$6:$B$17,$A112,'S6'!$E$6:$E$17,"Diego")+SUMIFS('S6'!$I$6:$I$17,'S6'!$B$6:$B$17,$A112,'S6'!$E$6:$E$17,"Ambos")+SUMIFS('S7'!$I$6:$I$19,'S7'!$B$6:$B$19,$A112,'S7'!$E$6:$E$19,"Diego")+SUMIFS('S7'!$I$6:$I$19,'S7'!$B$6:$B$19,$A112,'S7'!$E$6:$E$19,"Ambos")+SUMIFS('S8'!$I$6:$I$23,'S8'!$B$6:$B$23,$A112,'S8'!$E$6:$E$23,"Diego")+SUMIFS('S8'!$I$6:$I$23,'S8'!$B$6:$B$23,$A112,'S8'!$E$6:$E$23,"Ambos")+SUMIFS('S9'!$I$6:$I$15,'S9'!$B$6:$B$15,$A112,'S9'!$E$6:$E$15,"Diego")+SUMIFS('S9'!$I$6:$I$15,'S9'!$B$6:$B$15,$A112,'S9'!$E$6:$E$15,"Ambos")+SUMIFS('S10'!$I$6:$I$13,'S10'!$B$6:$B$13,$A112,'S10'!$E$6:$E$13,"Diego")+SUMIFS('S10'!$I$6:$I$13,'S10'!$B$6:$B$13,$A112,'S10'!$E$6:$E$13,"Ambos")+SUMIFS('Holgura'!$I$6:$I$11,'Holgura'!$B$6:$B$11,$A112,'Holgura'!$E$6:$E$11,"Diego")+SUMIFS('Holgura'!$I$6:$I$11,'Holgura'!$B$6:$B$11,$A112,'Holgura'!$E$6:$E$11,"Ambos")+SUMIFS('Entrega'!$I$6:$I$9,'Entrega'!$B$6:$B$9,$A112,'Entrega'!$E$6:$E$9,"Diego")+SUMIFS('Entrega'!$I$6:$I$9,'Entrega'!$B$6:$B$9,$A112,'Entrega'!$E$6:$E$9,"Ambos")+SUMIFS('Defensa'!$I$6:$I$10,'Defensa'!$B$6:$B$10,$A112,'Defensa'!$E$6:$E$10,"Diego")+SUMIFS('Defensa'!$I$6:$I$10,'Defensa'!$B$6:$B$10,$A112,'Defensa'!$E$6:$E$10,"Ambos")</f>
+        <f>SUMIFS('S1'!$I$6:$I$32,'S1'!$B$6:$B$32,$A112,'S1'!$E$6:$E$32,"Diego")+SUMIFS('S1'!$I$6:$I$32,'S1'!$B$6:$B$32,$A112,'S1'!$E$6:$E$32,"Ambos")+SUMIFS('S2'!$I$6:$I$23,'S2'!$B$6:$B$23,$A112,'S2'!$E$6:$E$23,"Diego")+SUMIFS('S2'!$I$6:$I$23,'S2'!$B$6:$B$23,$A112,'S2'!$E$6:$E$23,"Ambos")+SUMIFS('S3'!$I$6:$I$24,'S3'!$B$6:$B$24,$A112,'S3'!$E$6:$E$24,"Diego")+SUMIFS('S3'!$I$6:$I$24,'S3'!$B$6:$B$24,$A112,'S3'!$E$6:$E$24,"Ambos")+SUMIFS('S4'!$I$6:$I$22,'S4'!$B$6:$B$22,$A112,'S4'!$E$6:$E$22,"Diego")+SUMIFS('S4'!$I$6:$I$22,'S4'!$B$6:$B$22,$A112,'S4'!$E$6:$E$22,"Ambos")+SUMIFS('S5'!$I$6:$I$20,'S5'!$B$6:$B$20,$A112,'S5'!$E$6:$E$20,"Diego")+SUMIFS('S5'!$I$6:$I$20,'S5'!$B$6:$B$20,$A112,'S5'!$E$6:$E$20,"Ambos")+SUMIFS('S6'!$I$6:$I$17,'S6'!$B$6:$B$17,$A112,'S6'!$E$6:$E$17,"Diego")+SUMIFS('S6'!$I$6:$I$17,'S6'!$B$6:$B$17,$A112,'S6'!$E$6:$E$17,"Ambos")+SUMIFS('S7'!$I$6:$I$19,'S7'!$B$6:$B$19,$A112,'S7'!$E$6:$E$19,"Diego")+SUMIFS('S7'!$I$6:$I$19,'S7'!$B$6:$B$19,$A112,'S7'!$E$6:$E$19,"Ambos")+SUMIFS('S8'!$I$6:$I$23,'S8'!$B$6:$B$23,$A112,'S8'!$E$6:$E$23,"Diego")+SUMIFS('S8'!$I$6:$I$23,'S8'!$B$6:$B$23,$A112,'S8'!$E$6:$E$23,"Ambos")+SUMIFS('S9'!$I$6:$I$15,'S9'!$B$6:$B$15,$A112,'S9'!$E$6:$E$15,"Diego")+SUMIFS('S9'!$I$6:$I$15,'S9'!$B$6:$B$15,$A112,'S9'!$E$6:$E$15,"Ambos")+SUMIFS('S10'!$I$6:$I$13,'S10'!$B$6:$B$13,$A112,'S10'!$E$6:$E$13,"Diego")+SUMIFS('S10'!$I$6:$I$13,'S10'!$B$6:$B$13,$A112,'S10'!$E$6:$E$13,"Ambos")+SUMIFS('Holgura'!$I$6:$I$11,'Holgura'!$B$6:$B$11,$A112,'Holgura'!$E$6:$E$11,"Diego")+SUMIFS('Holgura'!$I$6:$I$11,'Holgura'!$B$6:$B$11,$A112,'Holgura'!$E$6:$E$11,"Ambos")+SUMIFS('Entrega'!$I$6:$I$9,'Entrega'!$B$6:$B$9,$A112,'Entrega'!$E$6:$E$9,"Diego")+SUMIFS('Entrega'!$I$6:$I$9,'Entrega'!$B$6:$B$9,$A112,'Entrega'!$E$6:$E$9,"Ambos")+SUMIFS('Defensa'!$I$6:$I$10,'Defensa'!$B$6:$B$10,$A112,'Defensa'!$E$6:$E$10,"Diego")+SUMIFS('Defensa'!$I$6:$I$10,'Defensa'!$B$6:$B$10,$A112,'Defensa'!$E$6:$E$10,"Ambos")</f>
         <v/>
       </c>
       <c r="F112" s="21">
-        <f>COUNTIFS('S1'!$B$6:$B$32,$A112,'S1'!$E$6:$E$32,"Víctor")+COUNTIFS('S1'!$B$6:$B$32,$A112,'S1'!$E$6:$E$32,"Ambos")+COUNTIFS('S2'!$B$6:$B$23,$A112,'S2'!$E$6:$E$23,"Víctor")+COUNTIFS('S2'!$B$6:$B$23,$A112,'S2'!$E$6:$E$23,"Ambos")+COUNTIFS('S3'!$B$6:$B$19,$A112,'S3'!$E$6:$E$19,"Víctor")+COUNTIFS('S3'!$B$6:$B$19,$A112,'S3'!$E$6:$E$19,"Ambos")+COUNTIFS('S4'!$B$6:$B$20,$A112,'S4'!$E$6:$E$20,"Víctor")+COUNTIFS('S4'!$B$6:$B$20,$A112,'S4'!$E$6:$E$20,"Ambos")+COUNTIFS('S5'!$B$6:$B$20,$A112,'S5'!$E$6:$E$20,"Víctor")+COUNTIFS('S5'!$B$6:$B$20,$A112,'S5'!$E$6:$E$20,"Ambos")+COUNTIFS('S6'!$B$6:$B$17,$A112,'S6'!$E$6:$E$17,"Víctor")+COUNTIFS('S6'!$B$6:$B$17,$A112,'S6'!$E$6:$E$17,"Ambos")+COUNTIFS('S7'!$B$6:$B$19,$A112,'S7'!$E$6:$E$19,"Víctor")+COUNTIFS('S7'!$B$6:$B$19,$A112,'S7'!$E$6:$E$19,"Ambos")+COUNTIFS('S8'!$B$6:$B$23,$A112,'S8'!$E$6:$E$23,"Víctor")+COUNTIFS('S8'!$B$6:$B$23,$A112,'S8'!$E$6:$E$23,"Ambos")+COUNTIFS('S9'!$B$6:$B$15,$A112,'S9'!$E$6:$E$15,"Víctor")+COUNTIFS('S9'!$B$6:$B$15,$A112,'S9'!$E$6:$E$15,"Ambos")+COUNTIFS('S10'!$B$6:$B$13,$A112,'S10'!$E$6:$E$13,"Víctor")+COUNTIFS('S10'!$B$6:$B$13,$A112,'S10'!$E$6:$E$13,"Ambos")+COUNTIFS('Holgura'!$B$6:$B$11,$A112,'Holgura'!$E$6:$E$11,"Víctor")+COUNTIFS('Holgura'!$B$6:$B$11,$A112,'Holgura'!$E$6:$E$11,"Ambos")+COUNTIFS('Entrega'!$B$6:$B$9,$A112,'Entrega'!$E$6:$E$9,"Víctor")+COUNTIFS('Entrega'!$B$6:$B$9,$A112,'Entrega'!$E$6:$E$9,"Ambos")+COUNTIFS('Defensa'!$B$6:$B$10,$A112,'Defensa'!$E$6:$E$10,"Víctor")+COUNTIFS('Defensa'!$B$6:$B$10,$A112,'Defensa'!$E$6:$E$10,"Ambos")</f>
+        <f>COUNTIFS('S1'!$B$6:$B$32,$A112,'S1'!$E$6:$E$32,"Víctor")+COUNTIFS('S1'!$B$6:$B$32,$A112,'S1'!$E$6:$E$32,"Ambos")+COUNTIFS('S2'!$B$6:$B$23,$A112,'S2'!$E$6:$E$23,"Víctor")+COUNTIFS('S2'!$B$6:$B$23,$A112,'S2'!$E$6:$E$23,"Ambos")+COUNTIFS('S3'!$B$6:$B$24,$A112,'S3'!$E$6:$E$24,"Víctor")+COUNTIFS('S3'!$B$6:$B$24,$A112,'S3'!$E$6:$E$24,"Ambos")+COUNTIFS('S4'!$B$6:$B$22,$A112,'S4'!$E$6:$E$22,"Víctor")+COUNTIFS('S4'!$B$6:$B$22,$A112,'S4'!$E$6:$E$22,"Ambos")+COUNTIFS('S5'!$B$6:$B$20,$A112,'S5'!$E$6:$E$20,"Víctor")+COUNTIFS('S5'!$B$6:$B$20,$A112,'S5'!$E$6:$E$20,"Ambos")+COUNTIFS('S6'!$B$6:$B$17,$A112,'S6'!$E$6:$E$17,"Víctor")+COUNTIFS('S6'!$B$6:$B$17,$A112,'S6'!$E$6:$E$17,"Ambos")+COUNTIFS('S7'!$B$6:$B$19,$A112,'S7'!$E$6:$E$19,"Víctor")+COUNTIFS('S7'!$B$6:$B$19,$A112,'S7'!$E$6:$E$19,"Ambos")+COUNTIFS('S8'!$B$6:$B$23,$A112,'S8'!$E$6:$E$23,"Víctor")+COUNTIFS('S8'!$B$6:$B$23,$A112,'S8'!$E$6:$E$23,"Ambos")+COUNTIFS('S9'!$B$6:$B$15,$A112,'S9'!$E$6:$E$15,"Víctor")+COUNTIFS('S9'!$B$6:$B$15,$A112,'S9'!$E$6:$E$15,"Ambos")+COUNTIFS('S10'!$B$6:$B$13,$A112,'S10'!$E$6:$E$13,"Víctor")+COUNTIFS('S10'!$B$6:$B$13,$A112,'S10'!$E$6:$E$13,"Ambos")+COUNTIFS('Holgura'!$B$6:$B$11,$A112,'Holgura'!$E$6:$E$11,"Víctor")+COUNTIFS('Holgura'!$B$6:$B$11,$A112,'Holgura'!$E$6:$E$11,"Ambos")+COUNTIFS('Entrega'!$B$6:$B$9,$A112,'Entrega'!$E$6:$E$9,"Víctor")+COUNTIFS('Entrega'!$B$6:$B$9,$A112,'Entrega'!$E$6:$E$9,"Ambos")+COUNTIFS('Defensa'!$B$6:$B$10,$A112,'Defensa'!$E$6:$E$10,"Víctor")+COUNTIFS('Defensa'!$B$6:$B$10,$A112,'Defensa'!$E$6:$E$10,"Ambos")</f>
         <v/>
       </c>
       <c r="G112" s="21">
-        <f>COUNTIFS('S1'!$B$6:$B$32,$A112,'S1'!$E$6:$E$32,"Diego")+COUNTIFS('S1'!$B$6:$B$32,$A112,'S1'!$E$6:$E$32,"Ambos")+COUNTIFS('S2'!$B$6:$B$23,$A112,'S2'!$E$6:$E$23,"Diego")+COUNTIFS('S2'!$B$6:$B$23,$A112,'S2'!$E$6:$E$23,"Ambos")+COUNTIFS('S3'!$B$6:$B$19,$A112,'S3'!$E$6:$E$19,"Diego")+COUNTIFS('S3'!$B$6:$B$19,$A112,'S3'!$E$6:$E$19,"Ambos")+COUNTIFS('S4'!$B$6:$B$20,$A112,'S4'!$E$6:$E$20,"Diego")+COUNTIFS('S4'!$B$6:$B$20,$A112,'S4'!$E$6:$E$20,"Ambos")+COUNTIFS('S5'!$B$6:$B$20,$A112,'S5'!$E$6:$E$20,"Diego")+COUNTIFS('S5'!$B$6:$B$20,$A112,'S5'!$E$6:$E$20,"Ambos")+COUNTIFS('S6'!$B$6:$B$17,$A112,'S6'!$E$6:$E$17,"Diego")+COUNTIFS('S6'!$B$6:$B$17,$A112,'S6'!$E$6:$E$17,"Ambos")+COUNTIFS('S7'!$B$6:$B$19,$A112,'S7'!$E$6:$E$19,"Diego")+COUNTIFS('S7'!$B$6:$B$19,$A112,'S7'!$E$6:$E$19,"Ambos")+COUNTIFS('S8'!$B$6:$B$23,$A112,'S8'!$E$6:$E$23,"Diego")+COUNTIFS('S8'!$B$6:$B$23,$A112,'S8'!$E$6:$E$23,"Ambos")+COUNTIFS('S9'!$B$6:$B$15,$A112,'S9'!$E$6:$E$15,"Diego")+COUNTIFS('S9'!$B$6:$B$15,$A112,'S9'!$E$6:$E$15,"Ambos")+COUNTIFS('S10'!$B$6:$B$13,$A112,'S10'!$E$6:$E$13,"Diego")+COUNTIFS('S10'!$B$6:$B$13,$A112,'S10'!$E$6:$E$13,"Ambos")+COUNTIFS('Holgura'!$B$6:$B$11,$A112,'Holgura'!$E$6:$E$11,"Diego")+COUNTIFS('Holgura'!$B$6:$B$11,$A112,'Holgura'!$E$6:$E$11,"Ambos")+COUNTIFS('Entrega'!$B$6:$B$9,$A112,'Entrega'!$E$6:$E$9,"Diego")+COUNTIFS('Entrega'!$B$6:$B$9,$A112,'Entrega'!$E$6:$E$9,"Ambos")+COUNTIFS('Defensa'!$B$6:$B$10,$A112,'Defensa'!$E$6:$E$10,"Diego")+COUNTIFS('Defensa'!$B$6:$B$10,$A112,'Defensa'!$E$6:$E$10,"Ambos")</f>
+        <f>COUNTIFS('S1'!$B$6:$B$32,$A112,'S1'!$E$6:$E$32,"Diego")+COUNTIFS('S1'!$B$6:$B$32,$A112,'S1'!$E$6:$E$32,"Ambos")+COUNTIFS('S2'!$B$6:$B$23,$A112,'S2'!$E$6:$E$23,"Diego")+COUNTIFS('S2'!$B$6:$B$23,$A112,'S2'!$E$6:$E$23,"Ambos")+COUNTIFS('S3'!$B$6:$B$24,$A112,'S3'!$E$6:$E$24,"Diego")+COUNTIFS('S3'!$B$6:$B$24,$A112,'S3'!$E$6:$E$24,"Ambos")+COUNTIFS('S4'!$B$6:$B$22,$A112,'S4'!$E$6:$E$22,"Diego")+COUNTIFS('S4'!$B$6:$B$22,$A112,'S4'!$E$6:$E$22,"Ambos")+COUNTIFS('S5'!$B$6:$B$20,$A112,'S5'!$E$6:$E$20,"Diego")+COUNTIFS('S5'!$B$6:$B$20,$A112,'S5'!$E$6:$E$20,"Ambos")+COUNTIFS('S6'!$B$6:$B$17,$A112,'S6'!$E$6:$E$17,"Diego")+COUNTIFS('S6'!$B$6:$B$17,$A112,'S6'!$E$6:$E$17,"Ambos")+COUNTIFS('S7'!$B$6:$B$19,$A112,'S7'!$E$6:$E$19,"Diego")+COUNTIFS('S7'!$B$6:$B$19,$A112,'S7'!$E$6:$E$19,"Ambos")+COUNTIFS('S8'!$B$6:$B$23,$A112,'S8'!$E$6:$E$23,"Diego")+COUNTIFS('S8'!$B$6:$B$23,$A112,'S8'!$E$6:$E$23,"Ambos")+COUNTIFS('S9'!$B$6:$B$15,$A112,'S9'!$E$6:$E$15,"Diego")+COUNTIFS('S9'!$B$6:$B$15,$A112,'S9'!$E$6:$E$15,"Ambos")+COUNTIFS('S10'!$B$6:$B$13,$A112,'S10'!$E$6:$E$13,"Diego")+COUNTIFS('S10'!$B$6:$B$13,$A112,'S10'!$E$6:$E$13,"Ambos")+COUNTIFS('Holgura'!$B$6:$B$11,$A112,'Holgura'!$E$6:$E$11,"Diego")+COUNTIFS('Holgura'!$B$6:$B$11,$A112,'Holgura'!$E$6:$E$11,"Ambos")+COUNTIFS('Entrega'!$B$6:$B$9,$A112,'Entrega'!$E$6:$E$9,"Diego")+COUNTIFS('Entrega'!$B$6:$B$9,$A112,'Entrega'!$E$6:$E$9,"Ambos")+COUNTIFS('Defensa'!$B$6:$B$10,$A112,'Defensa'!$E$6:$E$10,"Diego")+COUNTIFS('Defensa'!$B$6:$B$10,$A112,'Defensa'!$E$6:$E$10,"Ambos")</f>
         <v/>
       </c>
     </row>
@@ -11812,19 +11833,19 @@
         <v/>
       </c>
       <c r="D113" s="21">
-        <f>SUMIFS('S1'!$I$6:$I$32,'S1'!$B$6:$B$32,$A113,'S1'!$E$6:$E$32,"Víctor")+SUMIFS('S1'!$I$6:$I$32,'S1'!$B$6:$B$32,$A113,'S1'!$E$6:$E$32,"Ambos")+SUMIFS('S2'!$I$6:$I$23,'S2'!$B$6:$B$23,$A113,'S2'!$E$6:$E$23,"Víctor")+SUMIFS('S2'!$I$6:$I$23,'S2'!$B$6:$B$23,$A113,'S2'!$E$6:$E$23,"Ambos")+SUMIFS('S3'!$I$6:$I$19,'S3'!$B$6:$B$19,$A113,'S3'!$E$6:$E$19,"Víctor")+SUMIFS('S3'!$I$6:$I$19,'S3'!$B$6:$B$19,$A113,'S3'!$E$6:$E$19,"Ambos")+SUMIFS('S4'!$I$6:$I$20,'S4'!$B$6:$B$20,$A113,'S4'!$E$6:$E$20,"Víctor")+SUMIFS('S4'!$I$6:$I$20,'S4'!$B$6:$B$20,$A113,'S4'!$E$6:$E$20,"Ambos")+SUMIFS('S5'!$I$6:$I$20,'S5'!$B$6:$B$20,$A113,'S5'!$E$6:$E$20,"Víctor")+SUMIFS('S5'!$I$6:$I$20,'S5'!$B$6:$B$20,$A113,'S5'!$E$6:$E$20,"Ambos")+SUMIFS('S6'!$I$6:$I$17,'S6'!$B$6:$B$17,$A113,'S6'!$E$6:$E$17,"Víctor")+SUMIFS('S6'!$I$6:$I$17,'S6'!$B$6:$B$17,$A113,'S6'!$E$6:$E$17,"Ambos")+SUMIFS('S7'!$I$6:$I$19,'S7'!$B$6:$B$19,$A113,'S7'!$E$6:$E$19,"Víctor")+SUMIFS('S7'!$I$6:$I$19,'S7'!$B$6:$B$19,$A113,'S7'!$E$6:$E$19,"Ambos")+SUMIFS('S8'!$I$6:$I$23,'S8'!$B$6:$B$23,$A113,'S8'!$E$6:$E$23,"Víctor")+SUMIFS('S8'!$I$6:$I$23,'S8'!$B$6:$B$23,$A113,'S8'!$E$6:$E$23,"Ambos")+SUMIFS('S9'!$I$6:$I$15,'S9'!$B$6:$B$15,$A113,'S9'!$E$6:$E$15,"Víctor")+SUMIFS('S9'!$I$6:$I$15,'S9'!$B$6:$B$15,$A113,'S9'!$E$6:$E$15,"Ambos")+SUMIFS('S10'!$I$6:$I$13,'S10'!$B$6:$B$13,$A113,'S10'!$E$6:$E$13,"Víctor")+SUMIFS('S10'!$I$6:$I$13,'S10'!$B$6:$B$13,$A113,'S10'!$E$6:$E$13,"Ambos")+SUMIFS('Holgura'!$I$6:$I$11,'Holgura'!$B$6:$B$11,$A113,'Holgura'!$E$6:$E$11,"Víctor")+SUMIFS('Holgura'!$I$6:$I$11,'Holgura'!$B$6:$B$11,$A113,'Holgura'!$E$6:$E$11,"Ambos")+SUMIFS('Entrega'!$I$6:$I$9,'Entrega'!$B$6:$B$9,$A113,'Entrega'!$E$6:$E$9,"Víctor")+SUMIFS('Entrega'!$I$6:$I$9,'Entrega'!$B$6:$B$9,$A113,'Entrega'!$E$6:$E$9,"Ambos")+SUMIFS('Defensa'!$I$6:$I$10,'Defensa'!$B$6:$B$10,$A113,'Defensa'!$E$6:$E$10,"Víctor")+SUMIFS('Defensa'!$I$6:$I$10,'Defensa'!$B$6:$B$10,$A113,'Defensa'!$E$6:$E$10,"Ambos")</f>
+        <f>SUMIFS('S1'!$I$6:$I$32,'S1'!$B$6:$B$32,$A113,'S1'!$E$6:$E$32,"Víctor")+SUMIFS('S1'!$I$6:$I$32,'S1'!$B$6:$B$32,$A113,'S1'!$E$6:$E$32,"Ambos")+SUMIFS('S2'!$I$6:$I$23,'S2'!$B$6:$B$23,$A113,'S2'!$E$6:$E$23,"Víctor")+SUMIFS('S2'!$I$6:$I$23,'S2'!$B$6:$B$23,$A113,'S2'!$E$6:$E$23,"Ambos")+SUMIFS('S3'!$I$6:$I$24,'S3'!$B$6:$B$24,$A113,'S3'!$E$6:$E$24,"Víctor")+SUMIFS('S3'!$I$6:$I$24,'S3'!$B$6:$B$24,$A113,'S3'!$E$6:$E$24,"Ambos")+SUMIFS('S4'!$I$6:$I$22,'S4'!$B$6:$B$22,$A113,'S4'!$E$6:$E$22,"Víctor")+SUMIFS('S4'!$I$6:$I$22,'S4'!$B$6:$B$22,$A113,'S4'!$E$6:$E$22,"Ambos")+SUMIFS('S5'!$I$6:$I$20,'S5'!$B$6:$B$20,$A113,'S5'!$E$6:$E$20,"Víctor")+SUMIFS('S5'!$I$6:$I$20,'S5'!$B$6:$B$20,$A113,'S5'!$E$6:$E$20,"Ambos")+SUMIFS('S6'!$I$6:$I$17,'S6'!$B$6:$B$17,$A113,'S6'!$E$6:$E$17,"Víctor")+SUMIFS('S6'!$I$6:$I$17,'S6'!$B$6:$B$17,$A113,'S6'!$E$6:$E$17,"Ambos")+SUMIFS('S7'!$I$6:$I$19,'S7'!$B$6:$B$19,$A113,'S7'!$E$6:$E$19,"Víctor")+SUMIFS('S7'!$I$6:$I$19,'S7'!$B$6:$B$19,$A113,'S7'!$E$6:$E$19,"Ambos")+SUMIFS('S8'!$I$6:$I$23,'S8'!$B$6:$B$23,$A113,'S8'!$E$6:$E$23,"Víctor")+SUMIFS('S8'!$I$6:$I$23,'S8'!$B$6:$B$23,$A113,'S8'!$E$6:$E$23,"Ambos")+SUMIFS('S9'!$I$6:$I$15,'S9'!$B$6:$B$15,$A113,'S9'!$E$6:$E$15,"Víctor")+SUMIFS('S9'!$I$6:$I$15,'S9'!$B$6:$B$15,$A113,'S9'!$E$6:$E$15,"Ambos")+SUMIFS('S10'!$I$6:$I$13,'S10'!$B$6:$B$13,$A113,'S10'!$E$6:$E$13,"Víctor")+SUMIFS('S10'!$I$6:$I$13,'S10'!$B$6:$B$13,$A113,'S10'!$E$6:$E$13,"Ambos")+SUMIFS('Holgura'!$I$6:$I$11,'Holgura'!$B$6:$B$11,$A113,'Holgura'!$E$6:$E$11,"Víctor")+SUMIFS('Holgura'!$I$6:$I$11,'Holgura'!$B$6:$B$11,$A113,'Holgura'!$E$6:$E$11,"Ambos")+SUMIFS('Entrega'!$I$6:$I$9,'Entrega'!$B$6:$B$9,$A113,'Entrega'!$E$6:$E$9,"Víctor")+SUMIFS('Entrega'!$I$6:$I$9,'Entrega'!$B$6:$B$9,$A113,'Entrega'!$E$6:$E$9,"Ambos")+SUMIFS('Defensa'!$I$6:$I$10,'Defensa'!$B$6:$B$10,$A113,'Defensa'!$E$6:$E$10,"Víctor")+SUMIFS('Defensa'!$I$6:$I$10,'Defensa'!$B$6:$B$10,$A113,'Defensa'!$E$6:$E$10,"Ambos")</f>
         <v/>
       </c>
       <c r="E113" s="21">
-        <f>SUMIFS('S1'!$I$6:$I$32,'S1'!$B$6:$B$32,$A113,'S1'!$E$6:$E$32,"Diego")+SUMIFS('S1'!$I$6:$I$32,'S1'!$B$6:$B$32,$A113,'S1'!$E$6:$E$32,"Ambos")+SUMIFS('S2'!$I$6:$I$23,'S2'!$B$6:$B$23,$A113,'S2'!$E$6:$E$23,"Diego")+SUMIFS('S2'!$I$6:$I$23,'S2'!$B$6:$B$23,$A113,'S2'!$E$6:$E$23,"Ambos")+SUMIFS('S3'!$I$6:$I$19,'S3'!$B$6:$B$19,$A113,'S3'!$E$6:$E$19,"Diego")+SUMIFS('S3'!$I$6:$I$19,'S3'!$B$6:$B$19,$A113,'S3'!$E$6:$E$19,"Ambos")+SUMIFS('S4'!$I$6:$I$20,'S4'!$B$6:$B$20,$A113,'S4'!$E$6:$E$20,"Diego")+SUMIFS('S4'!$I$6:$I$20,'S4'!$B$6:$B$20,$A113,'S4'!$E$6:$E$20,"Ambos")+SUMIFS('S5'!$I$6:$I$20,'S5'!$B$6:$B$20,$A113,'S5'!$E$6:$E$20,"Diego")+SUMIFS('S5'!$I$6:$I$20,'S5'!$B$6:$B$20,$A113,'S5'!$E$6:$E$20,"Ambos")+SUMIFS('S6'!$I$6:$I$17,'S6'!$B$6:$B$17,$A113,'S6'!$E$6:$E$17,"Diego")+SUMIFS('S6'!$I$6:$I$17,'S6'!$B$6:$B$17,$A113,'S6'!$E$6:$E$17,"Ambos")+SUMIFS('S7'!$I$6:$I$19,'S7'!$B$6:$B$19,$A113,'S7'!$E$6:$E$19,"Diego")+SUMIFS('S7'!$I$6:$I$19,'S7'!$B$6:$B$19,$A113,'S7'!$E$6:$E$19,"Ambos")+SUMIFS('S8'!$I$6:$I$23,'S8'!$B$6:$B$23,$A113,'S8'!$E$6:$E$23,"Diego")+SUMIFS('S8'!$I$6:$I$23,'S8'!$B$6:$B$23,$A113,'S8'!$E$6:$E$23,"Ambos")+SUMIFS('S9'!$I$6:$I$15,'S9'!$B$6:$B$15,$A113,'S9'!$E$6:$E$15,"Diego")+SUMIFS('S9'!$I$6:$I$15,'S9'!$B$6:$B$15,$A113,'S9'!$E$6:$E$15,"Ambos")+SUMIFS('S10'!$I$6:$I$13,'S10'!$B$6:$B$13,$A113,'S10'!$E$6:$E$13,"Diego")+SUMIFS('S10'!$I$6:$I$13,'S10'!$B$6:$B$13,$A113,'S10'!$E$6:$E$13,"Ambos")+SUMIFS('Holgura'!$I$6:$I$11,'Holgura'!$B$6:$B$11,$A113,'Holgura'!$E$6:$E$11,"Diego")+SUMIFS('Holgura'!$I$6:$I$11,'Holgura'!$B$6:$B$11,$A113,'Holgura'!$E$6:$E$11,"Ambos")+SUMIFS('Entrega'!$I$6:$I$9,'Entrega'!$B$6:$B$9,$A113,'Entrega'!$E$6:$E$9,"Diego")+SUMIFS('Entrega'!$I$6:$I$9,'Entrega'!$B$6:$B$9,$A113,'Entrega'!$E$6:$E$9,"Ambos")+SUMIFS('Defensa'!$I$6:$I$10,'Defensa'!$B$6:$B$10,$A113,'Defensa'!$E$6:$E$10,"Diego")+SUMIFS('Defensa'!$I$6:$I$10,'Defensa'!$B$6:$B$10,$A113,'Defensa'!$E$6:$E$10,"Ambos")</f>
+        <f>SUMIFS('S1'!$I$6:$I$32,'S1'!$B$6:$B$32,$A113,'S1'!$E$6:$E$32,"Diego")+SUMIFS('S1'!$I$6:$I$32,'S1'!$B$6:$B$32,$A113,'S1'!$E$6:$E$32,"Ambos")+SUMIFS('S2'!$I$6:$I$23,'S2'!$B$6:$B$23,$A113,'S2'!$E$6:$E$23,"Diego")+SUMIFS('S2'!$I$6:$I$23,'S2'!$B$6:$B$23,$A113,'S2'!$E$6:$E$23,"Ambos")+SUMIFS('S3'!$I$6:$I$24,'S3'!$B$6:$B$24,$A113,'S3'!$E$6:$E$24,"Diego")+SUMIFS('S3'!$I$6:$I$24,'S3'!$B$6:$B$24,$A113,'S3'!$E$6:$E$24,"Ambos")+SUMIFS('S4'!$I$6:$I$22,'S4'!$B$6:$B$22,$A113,'S4'!$E$6:$E$22,"Diego")+SUMIFS('S4'!$I$6:$I$22,'S4'!$B$6:$B$22,$A113,'S4'!$E$6:$E$22,"Ambos")+SUMIFS('S5'!$I$6:$I$20,'S5'!$B$6:$B$20,$A113,'S5'!$E$6:$E$20,"Diego")+SUMIFS('S5'!$I$6:$I$20,'S5'!$B$6:$B$20,$A113,'S5'!$E$6:$E$20,"Ambos")+SUMIFS('S6'!$I$6:$I$17,'S6'!$B$6:$B$17,$A113,'S6'!$E$6:$E$17,"Diego")+SUMIFS('S6'!$I$6:$I$17,'S6'!$B$6:$B$17,$A113,'S6'!$E$6:$E$17,"Ambos")+SUMIFS('S7'!$I$6:$I$19,'S7'!$B$6:$B$19,$A113,'S7'!$E$6:$E$19,"Diego")+SUMIFS('S7'!$I$6:$I$19,'S7'!$B$6:$B$19,$A113,'S7'!$E$6:$E$19,"Ambos")+SUMIFS('S8'!$I$6:$I$23,'S8'!$B$6:$B$23,$A113,'S8'!$E$6:$E$23,"Diego")+SUMIFS('S8'!$I$6:$I$23,'S8'!$B$6:$B$23,$A113,'S8'!$E$6:$E$23,"Ambos")+SUMIFS('S9'!$I$6:$I$15,'S9'!$B$6:$B$15,$A113,'S9'!$E$6:$E$15,"Diego")+SUMIFS('S9'!$I$6:$I$15,'S9'!$B$6:$B$15,$A113,'S9'!$E$6:$E$15,"Ambos")+SUMIFS('S10'!$I$6:$I$13,'S10'!$B$6:$B$13,$A113,'S10'!$E$6:$E$13,"Diego")+SUMIFS('S10'!$I$6:$I$13,'S10'!$B$6:$B$13,$A113,'S10'!$E$6:$E$13,"Ambos")+SUMIFS('Holgura'!$I$6:$I$11,'Holgura'!$B$6:$B$11,$A113,'Holgura'!$E$6:$E$11,"Diego")+SUMIFS('Holgura'!$I$6:$I$11,'Holgura'!$B$6:$B$11,$A113,'Holgura'!$E$6:$E$11,"Ambos")+SUMIFS('Entrega'!$I$6:$I$9,'Entrega'!$B$6:$B$9,$A113,'Entrega'!$E$6:$E$9,"Diego")+SUMIFS('Entrega'!$I$6:$I$9,'Entrega'!$B$6:$B$9,$A113,'Entrega'!$E$6:$E$9,"Ambos")+SUMIFS('Defensa'!$I$6:$I$10,'Defensa'!$B$6:$B$10,$A113,'Defensa'!$E$6:$E$10,"Diego")+SUMIFS('Defensa'!$I$6:$I$10,'Defensa'!$B$6:$B$10,$A113,'Defensa'!$E$6:$E$10,"Ambos")</f>
         <v/>
       </c>
       <c r="F113" s="21">
-        <f>COUNTIFS('S1'!$B$6:$B$32,$A113,'S1'!$E$6:$E$32,"Víctor")+COUNTIFS('S1'!$B$6:$B$32,$A113,'S1'!$E$6:$E$32,"Ambos")+COUNTIFS('S2'!$B$6:$B$23,$A113,'S2'!$E$6:$E$23,"Víctor")+COUNTIFS('S2'!$B$6:$B$23,$A113,'S2'!$E$6:$E$23,"Ambos")+COUNTIFS('S3'!$B$6:$B$19,$A113,'S3'!$E$6:$E$19,"Víctor")+COUNTIFS('S3'!$B$6:$B$19,$A113,'S3'!$E$6:$E$19,"Ambos")+COUNTIFS('S4'!$B$6:$B$20,$A113,'S4'!$E$6:$E$20,"Víctor")+COUNTIFS('S4'!$B$6:$B$20,$A113,'S4'!$E$6:$E$20,"Ambos")+COUNTIFS('S5'!$B$6:$B$20,$A113,'S5'!$E$6:$E$20,"Víctor")+COUNTIFS('S5'!$B$6:$B$20,$A113,'S5'!$E$6:$E$20,"Ambos")+COUNTIFS('S6'!$B$6:$B$17,$A113,'S6'!$E$6:$E$17,"Víctor")+COUNTIFS('S6'!$B$6:$B$17,$A113,'S6'!$E$6:$E$17,"Ambos")+COUNTIFS('S7'!$B$6:$B$19,$A113,'S7'!$E$6:$E$19,"Víctor")+COUNTIFS('S7'!$B$6:$B$19,$A113,'S7'!$E$6:$E$19,"Ambos")+COUNTIFS('S8'!$B$6:$B$23,$A113,'S8'!$E$6:$E$23,"Víctor")+COUNTIFS('S8'!$B$6:$B$23,$A113,'S8'!$E$6:$E$23,"Ambos")+COUNTIFS('S9'!$B$6:$B$15,$A113,'S9'!$E$6:$E$15,"Víctor")+COUNTIFS('S9'!$B$6:$B$15,$A113,'S9'!$E$6:$E$15,"Ambos")+COUNTIFS('S10'!$B$6:$B$13,$A113,'S10'!$E$6:$E$13,"Víctor")+COUNTIFS('S10'!$B$6:$B$13,$A113,'S10'!$E$6:$E$13,"Ambos")+COUNTIFS('Holgura'!$B$6:$B$11,$A113,'Holgura'!$E$6:$E$11,"Víctor")+COUNTIFS('Holgura'!$B$6:$B$11,$A113,'Holgura'!$E$6:$E$11,"Ambos")+COUNTIFS('Entrega'!$B$6:$B$9,$A113,'Entrega'!$E$6:$E$9,"Víctor")+COUNTIFS('Entrega'!$B$6:$B$9,$A113,'Entrega'!$E$6:$E$9,"Ambos")+COUNTIFS('Defensa'!$B$6:$B$10,$A113,'Defensa'!$E$6:$E$10,"Víctor")+COUNTIFS('Defensa'!$B$6:$B$10,$A113,'Defensa'!$E$6:$E$10,"Ambos")</f>
+        <f>COUNTIFS('S1'!$B$6:$B$32,$A113,'S1'!$E$6:$E$32,"Víctor")+COUNTIFS('S1'!$B$6:$B$32,$A113,'S1'!$E$6:$E$32,"Ambos")+COUNTIFS('S2'!$B$6:$B$23,$A113,'S2'!$E$6:$E$23,"Víctor")+COUNTIFS('S2'!$B$6:$B$23,$A113,'S2'!$E$6:$E$23,"Ambos")+COUNTIFS('S3'!$B$6:$B$24,$A113,'S3'!$E$6:$E$24,"Víctor")+COUNTIFS('S3'!$B$6:$B$24,$A113,'S3'!$E$6:$E$24,"Ambos")+COUNTIFS('S4'!$B$6:$B$22,$A113,'S4'!$E$6:$E$22,"Víctor")+COUNTIFS('S4'!$B$6:$B$22,$A113,'S4'!$E$6:$E$22,"Ambos")+COUNTIFS('S5'!$B$6:$B$20,$A113,'S5'!$E$6:$E$20,"Víctor")+COUNTIFS('S5'!$B$6:$B$20,$A113,'S5'!$E$6:$E$20,"Ambos")+COUNTIFS('S6'!$B$6:$B$17,$A113,'S6'!$E$6:$E$17,"Víctor")+COUNTIFS('S6'!$B$6:$B$17,$A113,'S6'!$E$6:$E$17,"Ambos")+COUNTIFS('S7'!$B$6:$B$19,$A113,'S7'!$E$6:$E$19,"Víctor")+COUNTIFS('S7'!$B$6:$B$19,$A113,'S7'!$E$6:$E$19,"Ambos")+COUNTIFS('S8'!$B$6:$B$23,$A113,'S8'!$E$6:$E$23,"Víctor")+COUNTIFS('S8'!$B$6:$B$23,$A113,'S8'!$E$6:$E$23,"Ambos")+COUNTIFS('S9'!$B$6:$B$15,$A113,'S9'!$E$6:$E$15,"Víctor")+COUNTIFS('S9'!$B$6:$B$15,$A113,'S9'!$E$6:$E$15,"Ambos")+COUNTIFS('S10'!$B$6:$B$13,$A113,'S10'!$E$6:$E$13,"Víctor")+COUNTIFS('S10'!$B$6:$B$13,$A113,'S10'!$E$6:$E$13,"Ambos")+COUNTIFS('Holgura'!$B$6:$B$11,$A113,'Holgura'!$E$6:$E$11,"Víctor")+COUNTIFS('Holgura'!$B$6:$B$11,$A113,'Holgura'!$E$6:$E$11,"Ambos")+COUNTIFS('Entrega'!$B$6:$B$9,$A113,'Entrega'!$E$6:$E$9,"Víctor")+COUNTIFS('Entrega'!$B$6:$B$9,$A113,'Entrega'!$E$6:$E$9,"Ambos")+COUNTIFS('Defensa'!$B$6:$B$10,$A113,'Defensa'!$E$6:$E$10,"Víctor")+COUNTIFS('Defensa'!$B$6:$B$10,$A113,'Defensa'!$E$6:$E$10,"Ambos")</f>
         <v/>
       </c>
       <c r="G113" s="21">
-        <f>COUNTIFS('S1'!$B$6:$B$32,$A113,'S1'!$E$6:$E$32,"Diego")+COUNTIFS('S1'!$B$6:$B$32,$A113,'S1'!$E$6:$E$32,"Ambos")+COUNTIFS('S2'!$B$6:$B$23,$A113,'S2'!$E$6:$E$23,"Diego")+COUNTIFS('S2'!$B$6:$B$23,$A113,'S2'!$E$6:$E$23,"Ambos")+COUNTIFS('S3'!$B$6:$B$19,$A113,'S3'!$E$6:$E$19,"Diego")+COUNTIFS('S3'!$B$6:$B$19,$A113,'S3'!$E$6:$E$19,"Ambos")+COUNTIFS('S4'!$B$6:$B$20,$A113,'S4'!$E$6:$E$20,"Diego")+COUNTIFS('S4'!$B$6:$B$20,$A113,'S4'!$E$6:$E$20,"Ambos")+COUNTIFS('S5'!$B$6:$B$20,$A113,'S5'!$E$6:$E$20,"Diego")+COUNTIFS('S5'!$B$6:$B$20,$A113,'S5'!$E$6:$E$20,"Ambos")+COUNTIFS('S6'!$B$6:$B$17,$A113,'S6'!$E$6:$E$17,"Diego")+COUNTIFS('S6'!$B$6:$B$17,$A113,'S6'!$E$6:$E$17,"Ambos")+COUNTIFS('S7'!$B$6:$B$19,$A113,'S7'!$E$6:$E$19,"Diego")+COUNTIFS('S7'!$B$6:$B$19,$A113,'S7'!$E$6:$E$19,"Ambos")+COUNTIFS('S8'!$B$6:$B$23,$A113,'S8'!$E$6:$E$23,"Diego")+COUNTIFS('S8'!$B$6:$B$23,$A113,'S8'!$E$6:$E$23,"Ambos")+COUNTIFS('S9'!$B$6:$B$15,$A113,'S9'!$E$6:$E$15,"Diego")+COUNTIFS('S9'!$B$6:$B$15,$A113,'S9'!$E$6:$E$15,"Ambos")+COUNTIFS('S10'!$B$6:$B$13,$A113,'S10'!$E$6:$E$13,"Diego")+COUNTIFS('S10'!$B$6:$B$13,$A113,'S10'!$E$6:$E$13,"Ambos")+COUNTIFS('Holgura'!$B$6:$B$11,$A113,'Holgura'!$E$6:$E$11,"Diego")+COUNTIFS('Holgura'!$B$6:$B$11,$A113,'Holgura'!$E$6:$E$11,"Ambos")+COUNTIFS('Entrega'!$B$6:$B$9,$A113,'Entrega'!$E$6:$E$9,"Diego")+COUNTIFS('Entrega'!$B$6:$B$9,$A113,'Entrega'!$E$6:$E$9,"Ambos")+COUNTIFS('Defensa'!$B$6:$B$10,$A113,'Defensa'!$E$6:$E$10,"Diego")+COUNTIFS('Defensa'!$B$6:$B$10,$A113,'Defensa'!$E$6:$E$10,"Ambos")</f>
+        <f>COUNTIFS('S1'!$B$6:$B$32,$A113,'S1'!$E$6:$E$32,"Diego")+COUNTIFS('S1'!$B$6:$B$32,$A113,'S1'!$E$6:$E$32,"Ambos")+COUNTIFS('S2'!$B$6:$B$23,$A113,'S2'!$E$6:$E$23,"Diego")+COUNTIFS('S2'!$B$6:$B$23,$A113,'S2'!$E$6:$E$23,"Ambos")+COUNTIFS('S3'!$B$6:$B$24,$A113,'S3'!$E$6:$E$24,"Diego")+COUNTIFS('S3'!$B$6:$B$24,$A113,'S3'!$E$6:$E$24,"Ambos")+COUNTIFS('S4'!$B$6:$B$22,$A113,'S4'!$E$6:$E$22,"Diego")+COUNTIFS('S4'!$B$6:$B$22,$A113,'S4'!$E$6:$E$22,"Ambos")+COUNTIFS('S5'!$B$6:$B$20,$A113,'S5'!$E$6:$E$20,"Diego")+COUNTIFS('S5'!$B$6:$B$20,$A113,'S5'!$E$6:$E$20,"Ambos")+COUNTIFS('S6'!$B$6:$B$17,$A113,'S6'!$E$6:$E$17,"Diego")+COUNTIFS('S6'!$B$6:$B$17,$A113,'S6'!$E$6:$E$17,"Ambos")+COUNTIFS('S7'!$B$6:$B$19,$A113,'S7'!$E$6:$E$19,"Diego")+COUNTIFS('S7'!$B$6:$B$19,$A113,'S7'!$E$6:$E$19,"Ambos")+COUNTIFS('S8'!$B$6:$B$23,$A113,'S8'!$E$6:$E$23,"Diego")+COUNTIFS('S8'!$B$6:$B$23,$A113,'S8'!$E$6:$E$23,"Ambos")+COUNTIFS('S9'!$B$6:$B$15,$A113,'S9'!$E$6:$E$15,"Diego")+COUNTIFS('S9'!$B$6:$B$15,$A113,'S9'!$E$6:$E$15,"Ambos")+COUNTIFS('S10'!$B$6:$B$13,$A113,'S10'!$E$6:$E$13,"Diego")+COUNTIFS('S10'!$B$6:$B$13,$A113,'S10'!$E$6:$E$13,"Ambos")+COUNTIFS('Holgura'!$B$6:$B$11,$A113,'Holgura'!$E$6:$E$11,"Diego")+COUNTIFS('Holgura'!$B$6:$B$11,$A113,'Holgura'!$E$6:$E$11,"Ambos")+COUNTIFS('Entrega'!$B$6:$B$9,$A113,'Entrega'!$E$6:$E$9,"Diego")+COUNTIFS('Entrega'!$B$6:$B$9,$A113,'Entrega'!$E$6:$E$9,"Ambos")+COUNTIFS('Defensa'!$B$6:$B$10,$A113,'Defensa'!$E$6:$E$10,"Diego")+COUNTIFS('Defensa'!$B$6:$B$10,$A113,'Defensa'!$E$6:$E$10,"Ambos")</f>
         <v/>
       </c>
     </row>
@@ -11841,19 +11862,19 @@
         <v/>
       </c>
       <c r="D114" s="21">
-        <f>SUMIFS('S1'!$I$6:$I$32,'S1'!$B$6:$B$32,$A114,'S1'!$E$6:$E$32,"Víctor")+SUMIFS('S1'!$I$6:$I$32,'S1'!$B$6:$B$32,$A114,'S1'!$E$6:$E$32,"Ambos")+SUMIFS('S2'!$I$6:$I$23,'S2'!$B$6:$B$23,$A114,'S2'!$E$6:$E$23,"Víctor")+SUMIFS('S2'!$I$6:$I$23,'S2'!$B$6:$B$23,$A114,'S2'!$E$6:$E$23,"Ambos")+SUMIFS('S3'!$I$6:$I$19,'S3'!$B$6:$B$19,$A114,'S3'!$E$6:$E$19,"Víctor")+SUMIFS('S3'!$I$6:$I$19,'S3'!$B$6:$B$19,$A114,'S3'!$E$6:$E$19,"Ambos")+SUMIFS('S4'!$I$6:$I$20,'S4'!$B$6:$B$20,$A114,'S4'!$E$6:$E$20,"Víctor")+SUMIFS('S4'!$I$6:$I$20,'S4'!$B$6:$B$20,$A114,'S4'!$E$6:$E$20,"Ambos")+SUMIFS('S5'!$I$6:$I$20,'S5'!$B$6:$B$20,$A114,'S5'!$E$6:$E$20,"Víctor")+SUMIFS('S5'!$I$6:$I$20,'S5'!$B$6:$B$20,$A114,'S5'!$E$6:$E$20,"Ambos")+SUMIFS('S6'!$I$6:$I$17,'S6'!$B$6:$B$17,$A114,'S6'!$E$6:$E$17,"Víctor")+SUMIFS('S6'!$I$6:$I$17,'S6'!$B$6:$B$17,$A114,'S6'!$E$6:$E$17,"Ambos")+SUMIFS('S7'!$I$6:$I$19,'S7'!$B$6:$B$19,$A114,'S7'!$E$6:$E$19,"Víctor")+SUMIFS('S7'!$I$6:$I$19,'S7'!$B$6:$B$19,$A114,'S7'!$E$6:$E$19,"Ambos")+SUMIFS('S8'!$I$6:$I$23,'S8'!$B$6:$B$23,$A114,'S8'!$E$6:$E$23,"Víctor")+SUMIFS('S8'!$I$6:$I$23,'S8'!$B$6:$B$23,$A114,'S8'!$E$6:$E$23,"Ambos")+SUMIFS('S9'!$I$6:$I$15,'S9'!$B$6:$B$15,$A114,'S9'!$E$6:$E$15,"Víctor")+SUMIFS('S9'!$I$6:$I$15,'S9'!$B$6:$B$15,$A114,'S9'!$E$6:$E$15,"Ambos")+SUMIFS('S10'!$I$6:$I$13,'S10'!$B$6:$B$13,$A114,'S10'!$E$6:$E$13,"Víctor")+SUMIFS('S10'!$I$6:$I$13,'S10'!$B$6:$B$13,$A114,'S10'!$E$6:$E$13,"Ambos")+SUMIFS('Holgura'!$I$6:$I$11,'Holgura'!$B$6:$B$11,$A114,'Holgura'!$E$6:$E$11,"Víctor")+SUMIFS('Holgura'!$I$6:$I$11,'Holgura'!$B$6:$B$11,$A114,'Holgura'!$E$6:$E$11,"Ambos")+SUMIFS('Entrega'!$I$6:$I$9,'Entrega'!$B$6:$B$9,$A114,'Entrega'!$E$6:$E$9,"Víctor")+SUMIFS('Entrega'!$I$6:$I$9,'Entrega'!$B$6:$B$9,$A114,'Entrega'!$E$6:$E$9,"Ambos")+SUMIFS('Defensa'!$I$6:$I$10,'Defensa'!$B$6:$B$10,$A114,'Defensa'!$E$6:$E$10,"Víctor")+SUMIFS('Defensa'!$I$6:$I$10,'Defensa'!$B$6:$B$10,$A114,'Defensa'!$E$6:$E$10,"Ambos")</f>
+        <f>SUMIFS('S1'!$I$6:$I$32,'S1'!$B$6:$B$32,$A114,'S1'!$E$6:$E$32,"Víctor")+SUMIFS('S1'!$I$6:$I$32,'S1'!$B$6:$B$32,$A114,'S1'!$E$6:$E$32,"Ambos")+SUMIFS('S2'!$I$6:$I$23,'S2'!$B$6:$B$23,$A114,'S2'!$E$6:$E$23,"Víctor")+SUMIFS('S2'!$I$6:$I$23,'S2'!$B$6:$B$23,$A114,'S2'!$E$6:$E$23,"Ambos")+SUMIFS('S3'!$I$6:$I$24,'S3'!$B$6:$B$24,$A114,'S3'!$E$6:$E$24,"Víctor")+SUMIFS('S3'!$I$6:$I$24,'S3'!$B$6:$B$24,$A114,'S3'!$E$6:$E$24,"Ambos")+SUMIFS('S4'!$I$6:$I$22,'S4'!$B$6:$B$22,$A114,'S4'!$E$6:$E$22,"Víctor")+SUMIFS('S4'!$I$6:$I$22,'S4'!$B$6:$B$22,$A114,'S4'!$E$6:$E$22,"Ambos")+SUMIFS('S5'!$I$6:$I$20,'S5'!$B$6:$B$20,$A114,'S5'!$E$6:$E$20,"Víctor")+SUMIFS('S5'!$I$6:$I$20,'S5'!$B$6:$B$20,$A114,'S5'!$E$6:$E$20,"Ambos")+SUMIFS('S6'!$I$6:$I$17,'S6'!$B$6:$B$17,$A114,'S6'!$E$6:$E$17,"Víctor")+SUMIFS('S6'!$I$6:$I$17,'S6'!$B$6:$B$17,$A114,'S6'!$E$6:$E$17,"Ambos")+SUMIFS('S7'!$I$6:$I$19,'S7'!$B$6:$B$19,$A114,'S7'!$E$6:$E$19,"Víctor")+SUMIFS('S7'!$I$6:$I$19,'S7'!$B$6:$B$19,$A114,'S7'!$E$6:$E$19,"Ambos")+SUMIFS('S8'!$I$6:$I$23,'S8'!$B$6:$B$23,$A114,'S8'!$E$6:$E$23,"Víctor")+SUMIFS('S8'!$I$6:$I$23,'S8'!$B$6:$B$23,$A114,'S8'!$E$6:$E$23,"Ambos")+SUMIFS('S9'!$I$6:$I$15,'S9'!$B$6:$B$15,$A114,'S9'!$E$6:$E$15,"Víctor")+SUMIFS('S9'!$I$6:$I$15,'S9'!$B$6:$B$15,$A114,'S9'!$E$6:$E$15,"Ambos")+SUMIFS('S10'!$I$6:$I$13,'S10'!$B$6:$B$13,$A114,'S10'!$E$6:$E$13,"Víctor")+SUMIFS('S10'!$I$6:$I$13,'S10'!$B$6:$B$13,$A114,'S10'!$E$6:$E$13,"Ambos")+SUMIFS('Holgura'!$I$6:$I$11,'Holgura'!$B$6:$B$11,$A114,'Holgura'!$E$6:$E$11,"Víctor")+SUMIFS('Holgura'!$I$6:$I$11,'Holgura'!$B$6:$B$11,$A114,'Holgura'!$E$6:$E$11,"Ambos")+SUMIFS('Entrega'!$I$6:$I$9,'Entrega'!$B$6:$B$9,$A114,'Entrega'!$E$6:$E$9,"Víctor")+SUMIFS('Entrega'!$I$6:$I$9,'Entrega'!$B$6:$B$9,$A114,'Entrega'!$E$6:$E$9,"Ambos")+SUMIFS('Defensa'!$I$6:$I$10,'Defensa'!$B$6:$B$10,$A114,'Defensa'!$E$6:$E$10,"Víctor")+SUMIFS('Defensa'!$I$6:$I$10,'Defensa'!$B$6:$B$10,$A114,'Defensa'!$E$6:$E$10,"Ambos")</f>
         <v/>
       </c>
       <c r="E114" s="21">
-        <f>SUMIFS('S1'!$I$6:$I$32,'S1'!$B$6:$B$32,$A114,'S1'!$E$6:$E$32,"Diego")+SUMIFS('S1'!$I$6:$I$32,'S1'!$B$6:$B$32,$A114,'S1'!$E$6:$E$32,"Ambos")+SUMIFS('S2'!$I$6:$I$23,'S2'!$B$6:$B$23,$A114,'S2'!$E$6:$E$23,"Diego")+SUMIFS('S2'!$I$6:$I$23,'S2'!$B$6:$B$23,$A114,'S2'!$E$6:$E$23,"Ambos")+SUMIFS('S3'!$I$6:$I$19,'S3'!$B$6:$B$19,$A114,'S3'!$E$6:$E$19,"Diego")+SUMIFS('S3'!$I$6:$I$19,'S3'!$B$6:$B$19,$A114,'S3'!$E$6:$E$19,"Ambos")+SUMIFS('S4'!$I$6:$I$20,'S4'!$B$6:$B$20,$A114,'S4'!$E$6:$E$20,"Diego")+SUMIFS('S4'!$I$6:$I$20,'S4'!$B$6:$B$20,$A114,'S4'!$E$6:$E$20,"Ambos")+SUMIFS('S5'!$I$6:$I$20,'S5'!$B$6:$B$20,$A114,'S5'!$E$6:$E$20,"Diego")+SUMIFS('S5'!$I$6:$I$20,'S5'!$B$6:$B$20,$A114,'S5'!$E$6:$E$20,"Ambos")+SUMIFS('S6'!$I$6:$I$17,'S6'!$B$6:$B$17,$A114,'S6'!$E$6:$E$17,"Diego")+SUMIFS('S6'!$I$6:$I$17,'S6'!$B$6:$B$17,$A114,'S6'!$E$6:$E$17,"Ambos")+SUMIFS('S7'!$I$6:$I$19,'S7'!$B$6:$B$19,$A114,'S7'!$E$6:$E$19,"Diego")+SUMIFS('S7'!$I$6:$I$19,'S7'!$B$6:$B$19,$A114,'S7'!$E$6:$E$19,"Ambos")+SUMIFS('S8'!$I$6:$I$23,'S8'!$B$6:$B$23,$A114,'S8'!$E$6:$E$23,"Diego")+SUMIFS('S8'!$I$6:$I$23,'S8'!$B$6:$B$23,$A114,'S8'!$E$6:$E$23,"Ambos")+SUMIFS('S9'!$I$6:$I$15,'S9'!$B$6:$B$15,$A114,'S9'!$E$6:$E$15,"Diego")+SUMIFS('S9'!$I$6:$I$15,'S9'!$B$6:$B$15,$A114,'S9'!$E$6:$E$15,"Ambos")+SUMIFS('S10'!$I$6:$I$13,'S10'!$B$6:$B$13,$A114,'S10'!$E$6:$E$13,"Diego")+SUMIFS('S10'!$I$6:$I$13,'S10'!$B$6:$B$13,$A114,'S10'!$E$6:$E$13,"Ambos")+SUMIFS('Holgura'!$I$6:$I$11,'Holgura'!$B$6:$B$11,$A114,'Holgura'!$E$6:$E$11,"Diego")+SUMIFS('Holgura'!$I$6:$I$11,'Holgura'!$B$6:$B$11,$A114,'Holgura'!$E$6:$E$11,"Ambos")+SUMIFS('Entrega'!$I$6:$I$9,'Entrega'!$B$6:$B$9,$A114,'Entrega'!$E$6:$E$9,"Diego")+SUMIFS('Entrega'!$I$6:$I$9,'Entrega'!$B$6:$B$9,$A114,'Entrega'!$E$6:$E$9,"Ambos")+SUMIFS('Defensa'!$I$6:$I$10,'Defensa'!$B$6:$B$10,$A114,'Defensa'!$E$6:$E$10,"Diego")+SUMIFS('Defensa'!$I$6:$I$10,'Defensa'!$B$6:$B$10,$A114,'Defensa'!$E$6:$E$10,"Ambos")</f>
+        <f>SUMIFS('S1'!$I$6:$I$32,'S1'!$B$6:$B$32,$A114,'S1'!$E$6:$E$32,"Diego")+SUMIFS('S1'!$I$6:$I$32,'S1'!$B$6:$B$32,$A114,'S1'!$E$6:$E$32,"Ambos")+SUMIFS('S2'!$I$6:$I$23,'S2'!$B$6:$B$23,$A114,'S2'!$E$6:$E$23,"Diego")+SUMIFS('S2'!$I$6:$I$23,'S2'!$B$6:$B$23,$A114,'S2'!$E$6:$E$23,"Ambos")+SUMIFS('S3'!$I$6:$I$24,'S3'!$B$6:$B$24,$A114,'S3'!$E$6:$E$24,"Diego")+SUMIFS('S3'!$I$6:$I$24,'S3'!$B$6:$B$24,$A114,'S3'!$E$6:$E$24,"Ambos")+SUMIFS('S4'!$I$6:$I$22,'S4'!$B$6:$B$22,$A114,'S4'!$E$6:$E$22,"Diego")+SUMIFS('S4'!$I$6:$I$22,'S4'!$B$6:$B$22,$A114,'S4'!$E$6:$E$22,"Ambos")+SUMIFS('S5'!$I$6:$I$20,'S5'!$B$6:$B$20,$A114,'S5'!$E$6:$E$20,"Diego")+SUMIFS('S5'!$I$6:$I$20,'S5'!$B$6:$B$20,$A114,'S5'!$E$6:$E$20,"Ambos")+SUMIFS('S6'!$I$6:$I$17,'S6'!$B$6:$B$17,$A114,'S6'!$E$6:$E$17,"Diego")+SUMIFS('S6'!$I$6:$I$17,'S6'!$B$6:$B$17,$A114,'S6'!$E$6:$E$17,"Ambos")+SUMIFS('S7'!$I$6:$I$19,'S7'!$B$6:$B$19,$A114,'S7'!$E$6:$E$19,"Diego")+SUMIFS('S7'!$I$6:$I$19,'S7'!$B$6:$B$19,$A114,'S7'!$E$6:$E$19,"Ambos")+SUMIFS('S8'!$I$6:$I$23,'S8'!$B$6:$B$23,$A114,'S8'!$E$6:$E$23,"Diego")+SUMIFS('S8'!$I$6:$I$23,'S8'!$B$6:$B$23,$A114,'S8'!$E$6:$E$23,"Ambos")+SUMIFS('S9'!$I$6:$I$15,'S9'!$B$6:$B$15,$A114,'S9'!$E$6:$E$15,"Diego")+SUMIFS('S9'!$I$6:$I$15,'S9'!$B$6:$B$15,$A114,'S9'!$E$6:$E$15,"Ambos")+SUMIFS('S10'!$I$6:$I$13,'S10'!$B$6:$B$13,$A114,'S10'!$E$6:$E$13,"Diego")+SUMIFS('S10'!$I$6:$I$13,'S10'!$B$6:$B$13,$A114,'S10'!$E$6:$E$13,"Ambos")+SUMIFS('Holgura'!$I$6:$I$11,'Holgura'!$B$6:$B$11,$A114,'Holgura'!$E$6:$E$11,"Diego")+SUMIFS('Holgura'!$I$6:$I$11,'Holgura'!$B$6:$B$11,$A114,'Holgura'!$E$6:$E$11,"Ambos")+SUMIFS('Entrega'!$I$6:$I$9,'Entrega'!$B$6:$B$9,$A114,'Entrega'!$E$6:$E$9,"Diego")+SUMIFS('Entrega'!$I$6:$I$9,'Entrega'!$B$6:$B$9,$A114,'Entrega'!$E$6:$E$9,"Ambos")+SUMIFS('Defensa'!$I$6:$I$10,'Defensa'!$B$6:$B$10,$A114,'Defensa'!$E$6:$E$10,"Diego")+SUMIFS('Defensa'!$I$6:$I$10,'Defensa'!$B$6:$B$10,$A114,'Defensa'!$E$6:$E$10,"Ambos")</f>
         <v/>
       </c>
       <c r="F114" s="21">
-        <f>COUNTIFS('S1'!$B$6:$B$32,$A114,'S1'!$E$6:$E$32,"Víctor")+COUNTIFS('S1'!$B$6:$B$32,$A114,'S1'!$E$6:$E$32,"Ambos")+COUNTIFS('S2'!$B$6:$B$23,$A114,'S2'!$E$6:$E$23,"Víctor")+COUNTIFS('S2'!$B$6:$B$23,$A114,'S2'!$E$6:$E$23,"Ambos")+COUNTIFS('S3'!$B$6:$B$19,$A114,'S3'!$E$6:$E$19,"Víctor")+COUNTIFS('S3'!$B$6:$B$19,$A114,'S3'!$E$6:$E$19,"Ambos")+COUNTIFS('S4'!$B$6:$B$20,$A114,'S4'!$E$6:$E$20,"Víctor")+COUNTIFS('S4'!$B$6:$B$20,$A114,'S4'!$E$6:$E$20,"Ambos")+COUNTIFS('S5'!$B$6:$B$20,$A114,'S5'!$E$6:$E$20,"Víctor")+COUNTIFS('S5'!$B$6:$B$20,$A114,'S5'!$E$6:$E$20,"Ambos")+COUNTIFS('S6'!$B$6:$B$17,$A114,'S6'!$E$6:$E$17,"Víctor")+COUNTIFS('S6'!$B$6:$B$17,$A114,'S6'!$E$6:$E$17,"Ambos")+COUNTIFS('S7'!$B$6:$B$19,$A114,'S7'!$E$6:$E$19,"Víctor")+COUNTIFS('S7'!$B$6:$B$19,$A114,'S7'!$E$6:$E$19,"Ambos")+COUNTIFS('S8'!$B$6:$B$23,$A114,'S8'!$E$6:$E$23,"Víctor")+COUNTIFS('S8'!$B$6:$B$23,$A114,'S8'!$E$6:$E$23,"Ambos")+COUNTIFS('S9'!$B$6:$B$15,$A114,'S9'!$E$6:$E$15,"Víctor")+COUNTIFS('S9'!$B$6:$B$15,$A114,'S9'!$E$6:$E$15,"Ambos")+COUNTIFS('S10'!$B$6:$B$13,$A114,'S10'!$E$6:$E$13,"Víctor")+COUNTIFS('S10'!$B$6:$B$13,$A114,'S10'!$E$6:$E$13,"Ambos")+COUNTIFS('Holgura'!$B$6:$B$11,$A114,'Holgura'!$E$6:$E$11,"Víctor")+COUNTIFS('Holgura'!$B$6:$B$11,$A114,'Holgura'!$E$6:$E$11,"Ambos")+COUNTIFS('Entrega'!$B$6:$B$9,$A114,'Entrega'!$E$6:$E$9,"Víctor")+COUNTIFS('Entrega'!$B$6:$B$9,$A114,'Entrega'!$E$6:$E$9,"Ambos")+COUNTIFS('Defensa'!$B$6:$B$10,$A114,'Defensa'!$E$6:$E$10,"Víctor")+COUNTIFS('Defensa'!$B$6:$B$10,$A114,'Defensa'!$E$6:$E$10,"Ambos")</f>
+        <f>COUNTIFS('S1'!$B$6:$B$32,$A114,'S1'!$E$6:$E$32,"Víctor")+COUNTIFS('S1'!$B$6:$B$32,$A114,'S1'!$E$6:$E$32,"Ambos")+COUNTIFS('S2'!$B$6:$B$23,$A114,'S2'!$E$6:$E$23,"Víctor")+COUNTIFS('S2'!$B$6:$B$23,$A114,'S2'!$E$6:$E$23,"Ambos")+COUNTIFS('S3'!$B$6:$B$24,$A114,'S3'!$E$6:$E$24,"Víctor")+COUNTIFS('S3'!$B$6:$B$24,$A114,'S3'!$E$6:$E$24,"Ambos")+COUNTIFS('S4'!$B$6:$B$22,$A114,'S4'!$E$6:$E$22,"Víctor")+COUNTIFS('S4'!$B$6:$B$22,$A114,'S4'!$E$6:$E$22,"Ambos")+COUNTIFS('S5'!$B$6:$B$20,$A114,'S5'!$E$6:$E$20,"Víctor")+COUNTIFS('S5'!$B$6:$B$20,$A114,'S5'!$E$6:$E$20,"Ambos")+COUNTIFS('S6'!$B$6:$B$17,$A114,'S6'!$E$6:$E$17,"Víctor")+COUNTIFS('S6'!$B$6:$B$17,$A114,'S6'!$E$6:$E$17,"Ambos")+COUNTIFS('S7'!$B$6:$B$19,$A114,'S7'!$E$6:$E$19,"Víctor")+COUNTIFS('S7'!$B$6:$B$19,$A114,'S7'!$E$6:$E$19,"Ambos")+COUNTIFS('S8'!$B$6:$B$23,$A114,'S8'!$E$6:$E$23,"Víctor")+COUNTIFS('S8'!$B$6:$B$23,$A114,'S8'!$E$6:$E$23,"Ambos")+COUNTIFS('S9'!$B$6:$B$15,$A114,'S9'!$E$6:$E$15,"Víctor")+COUNTIFS('S9'!$B$6:$B$15,$A114,'S9'!$E$6:$E$15,"Ambos")+COUNTIFS('S10'!$B$6:$B$13,$A114,'S10'!$E$6:$E$13,"Víctor")+COUNTIFS('S10'!$B$6:$B$13,$A114,'S10'!$E$6:$E$13,"Ambos")+COUNTIFS('Holgura'!$B$6:$B$11,$A114,'Holgura'!$E$6:$E$11,"Víctor")+COUNTIFS('Holgura'!$B$6:$B$11,$A114,'Holgura'!$E$6:$E$11,"Ambos")+COUNTIFS('Entrega'!$B$6:$B$9,$A114,'Entrega'!$E$6:$E$9,"Víctor")+COUNTIFS('Entrega'!$B$6:$B$9,$A114,'Entrega'!$E$6:$E$9,"Ambos")+COUNTIFS('Defensa'!$B$6:$B$10,$A114,'Defensa'!$E$6:$E$10,"Víctor")+COUNTIFS('Defensa'!$B$6:$B$10,$A114,'Defensa'!$E$6:$E$10,"Ambos")</f>
         <v/>
       </c>
       <c r="G114" s="21">
-        <f>COUNTIFS('S1'!$B$6:$B$32,$A114,'S1'!$E$6:$E$32,"Diego")+COUNTIFS('S1'!$B$6:$B$32,$A114,'S1'!$E$6:$E$32,"Ambos")+COUNTIFS('S2'!$B$6:$B$23,$A114,'S2'!$E$6:$E$23,"Diego")+COUNTIFS('S2'!$B$6:$B$23,$A114,'S2'!$E$6:$E$23,"Ambos")+COUNTIFS('S3'!$B$6:$B$19,$A114,'S3'!$E$6:$E$19,"Diego")+COUNTIFS('S3'!$B$6:$B$19,$A114,'S3'!$E$6:$E$19,"Ambos")+COUNTIFS('S4'!$B$6:$B$20,$A114,'S4'!$E$6:$E$20,"Diego")+COUNTIFS('S4'!$B$6:$B$20,$A114,'S4'!$E$6:$E$20,"Ambos")+COUNTIFS('S5'!$B$6:$B$20,$A114,'S5'!$E$6:$E$20,"Diego")+COUNTIFS('S5'!$B$6:$B$20,$A114,'S5'!$E$6:$E$20,"Ambos")+COUNTIFS('S6'!$B$6:$B$17,$A114,'S6'!$E$6:$E$17,"Diego")+COUNTIFS('S6'!$B$6:$B$17,$A114,'S6'!$E$6:$E$17,"Ambos")+COUNTIFS('S7'!$B$6:$B$19,$A114,'S7'!$E$6:$E$19,"Diego")+COUNTIFS('S7'!$B$6:$B$19,$A114,'S7'!$E$6:$E$19,"Ambos")+COUNTIFS('S8'!$B$6:$B$23,$A114,'S8'!$E$6:$E$23,"Diego")+COUNTIFS('S8'!$B$6:$B$23,$A114,'S8'!$E$6:$E$23,"Ambos")+COUNTIFS('S9'!$B$6:$B$15,$A114,'S9'!$E$6:$E$15,"Diego")+COUNTIFS('S9'!$B$6:$B$15,$A114,'S9'!$E$6:$E$15,"Ambos")+COUNTIFS('S10'!$B$6:$B$13,$A114,'S10'!$E$6:$E$13,"Diego")+COUNTIFS('S10'!$B$6:$B$13,$A114,'S10'!$E$6:$E$13,"Ambos")+COUNTIFS('Holgura'!$B$6:$B$11,$A114,'Holgura'!$E$6:$E$11,"Diego")+COUNTIFS('Holgura'!$B$6:$B$11,$A114,'Holgura'!$E$6:$E$11,"Ambos")+COUNTIFS('Entrega'!$B$6:$B$9,$A114,'Entrega'!$E$6:$E$9,"Diego")+COUNTIFS('Entrega'!$B$6:$B$9,$A114,'Entrega'!$E$6:$E$9,"Ambos")+COUNTIFS('Defensa'!$B$6:$B$10,$A114,'Defensa'!$E$6:$E$10,"Diego")+COUNTIFS('Defensa'!$B$6:$B$10,$A114,'Defensa'!$E$6:$E$10,"Ambos")</f>
+        <f>COUNTIFS('S1'!$B$6:$B$32,$A114,'S1'!$E$6:$E$32,"Diego")+COUNTIFS('S1'!$B$6:$B$32,$A114,'S1'!$E$6:$E$32,"Ambos")+COUNTIFS('S2'!$B$6:$B$23,$A114,'S2'!$E$6:$E$23,"Diego")+COUNTIFS('S2'!$B$6:$B$23,$A114,'S2'!$E$6:$E$23,"Ambos")+COUNTIFS('S3'!$B$6:$B$24,$A114,'S3'!$E$6:$E$24,"Diego")+COUNTIFS('S3'!$B$6:$B$24,$A114,'S3'!$E$6:$E$24,"Ambos")+COUNTIFS('S4'!$B$6:$B$22,$A114,'S4'!$E$6:$E$22,"Diego")+COUNTIFS('S4'!$B$6:$B$22,$A114,'S4'!$E$6:$E$22,"Ambos")+COUNTIFS('S5'!$B$6:$B$20,$A114,'S5'!$E$6:$E$20,"Diego")+COUNTIFS('S5'!$B$6:$B$20,$A114,'S5'!$E$6:$E$20,"Ambos")+COUNTIFS('S6'!$B$6:$B$17,$A114,'S6'!$E$6:$E$17,"Diego")+COUNTIFS('S6'!$B$6:$B$17,$A114,'S6'!$E$6:$E$17,"Ambos")+COUNTIFS('S7'!$B$6:$B$19,$A114,'S7'!$E$6:$E$19,"Diego")+COUNTIFS('S7'!$B$6:$B$19,$A114,'S7'!$E$6:$E$19,"Ambos")+COUNTIFS('S8'!$B$6:$B$23,$A114,'S8'!$E$6:$E$23,"Diego")+COUNTIFS('S8'!$B$6:$B$23,$A114,'S8'!$E$6:$E$23,"Ambos")+COUNTIFS('S9'!$B$6:$B$15,$A114,'S9'!$E$6:$E$15,"Diego")+COUNTIFS('S9'!$B$6:$B$15,$A114,'S9'!$E$6:$E$15,"Ambos")+COUNTIFS('S10'!$B$6:$B$13,$A114,'S10'!$E$6:$E$13,"Diego")+COUNTIFS('S10'!$B$6:$B$13,$A114,'S10'!$E$6:$E$13,"Ambos")+COUNTIFS('Holgura'!$B$6:$B$11,$A114,'Holgura'!$E$6:$E$11,"Diego")+COUNTIFS('Holgura'!$B$6:$B$11,$A114,'Holgura'!$E$6:$E$11,"Ambos")+COUNTIFS('Entrega'!$B$6:$B$9,$A114,'Entrega'!$E$6:$E$9,"Diego")+COUNTIFS('Entrega'!$B$6:$B$9,$A114,'Entrega'!$E$6:$E$9,"Ambos")+COUNTIFS('Defensa'!$B$6:$B$10,$A114,'Defensa'!$E$6:$E$10,"Diego")+COUNTIFS('Defensa'!$B$6:$B$10,$A114,'Defensa'!$E$6:$E$10,"Ambos")</f>
         <v/>
       </c>
     </row>
@@ -11870,19 +11891,19 @@
         <v/>
       </c>
       <c r="D115" s="21">
-        <f>SUMIFS('S1'!$I$6:$I$32,'S1'!$B$6:$B$32,$A115,'S1'!$E$6:$E$32,"Víctor")+SUMIFS('S1'!$I$6:$I$32,'S1'!$B$6:$B$32,$A115,'S1'!$E$6:$E$32,"Ambos")+SUMIFS('S2'!$I$6:$I$23,'S2'!$B$6:$B$23,$A115,'S2'!$E$6:$E$23,"Víctor")+SUMIFS('S2'!$I$6:$I$23,'S2'!$B$6:$B$23,$A115,'S2'!$E$6:$E$23,"Ambos")+SUMIFS('S3'!$I$6:$I$19,'S3'!$B$6:$B$19,$A115,'S3'!$E$6:$E$19,"Víctor")+SUMIFS('S3'!$I$6:$I$19,'S3'!$B$6:$B$19,$A115,'S3'!$E$6:$E$19,"Ambos")+SUMIFS('S4'!$I$6:$I$20,'S4'!$B$6:$B$20,$A115,'S4'!$E$6:$E$20,"Víctor")+SUMIFS('S4'!$I$6:$I$20,'S4'!$B$6:$B$20,$A115,'S4'!$E$6:$E$20,"Ambos")+SUMIFS('S5'!$I$6:$I$20,'S5'!$B$6:$B$20,$A115,'S5'!$E$6:$E$20,"Víctor")+SUMIFS('S5'!$I$6:$I$20,'S5'!$B$6:$B$20,$A115,'S5'!$E$6:$E$20,"Ambos")+SUMIFS('S6'!$I$6:$I$17,'S6'!$B$6:$B$17,$A115,'S6'!$E$6:$E$17,"Víctor")+SUMIFS('S6'!$I$6:$I$17,'S6'!$B$6:$B$17,$A115,'S6'!$E$6:$E$17,"Ambos")+SUMIFS('S7'!$I$6:$I$19,'S7'!$B$6:$B$19,$A115,'S7'!$E$6:$E$19,"Víctor")+SUMIFS('S7'!$I$6:$I$19,'S7'!$B$6:$B$19,$A115,'S7'!$E$6:$E$19,"Ambos")+SUMIFS('S8'!$I$6:$I$23,'S8'!$B$6:$B$23,$A115,'S8'!$E$6:$E$23,"Víctor")+SUMIFS('S8'!$I$6:$I$23,'S8'!$B$6:$B$23,$A115,'S8'!$E$6:$E$23,"Ambos")+SUMIFS('S9'!$I$6:$I$15,'S9'!$B$6:$B$15,$A115,'S9'!$E$6:$E$15,"Víctor")+SUMIFS('S9'!$I$6:$I$15,'S9'!$B$6:$B$15,$A115,'S9'!$E$6:$E$15,"Ambos")+SUMIFS('S10'!$I$6:$I$13,'S10'!$B$6:$B$13,$A115,'S10'!$E$6:$E$13,"Víctor")+SUMIFS('S10'!$I$6:$I$13,'S10'!$B$6:$B$13,$A115,'S10'!$E$6:$E$13,"Ambos")+SUMIFS('Holgura'!$I$6:$I$11,'Holgura'!$B$6:$B$11,$A115,'Holgura'!$E$6:$E$11,"Víctor")+SUMIFS('Holgura'!$I$6:$I$11,'Holgura'!$B$6:$B$11,$A115,'Holgura'!$E$6:$E$11,"Ambos")+SUMIFS('Entrega'!$I$6:$I$9,'Entrega'!$B$6:$B$9,$A115,'Entrega'!$E$6:$E$9,"Víctor")+SUMIFS('Entrega'!$I$6:$I$9,'Entrega'!$B$6:$B$9,$A115,'Entrega'!$E$6:$E$9,"Ambos")+SUMIFS('Defensa'!$I$6:$I$10,'Defensa'!$B$6:$B$10,$A115,'Defensa'!$E$6:$E$10,"Víctor")+SUMIFS('Defensa'!$I$6:$I$10,'Defensa'!$B$6:$B$10,$A115,'Defensa'!$E$6:$E$10,"Ambos")</f>
+        <f>SUMIFS('S1'!$I$6:$I$32,'S1'!$B$6:$B$32,$A115,'S1'!$E$6:$E$32,"Víctor")+SUMIFS('S1'!$I$6:$I$32,'S1'!$B$6:$B$32,$A115,'S1'!$E$6:$E$32,"Ambos")+SUMIFS('S2'!$I$6:$I$23,'S2'!$B$6:$B$23,$A115,'S2'!$E$6:$E$23,"Víctor")+SUMIFS('S2'!$I$6:$I$23,'S2'!$B$6:$B$23,$A115,'S2'!$E$6:$E$23,"Ambos")+SUMIFS('S3'!$I$6:$I$24,'S3'!$B$6:$B$24,$A115,'S3'!$E$6:$E$24,"Víctor")+SUMIFS('S3'!$I$6:$I$24,'S3'!$B$6:$B$24,$A115,'S3'!$E$6:$E$24,"Ambos")+SUMIFS('S4'!$I$6:$I$22,'S4'!$B$6:$B$22,$A115,'S4'!$E$6:$E$22,"Víctor")+SUMIFS('S4'!$I$6:$I$22,'S4'!$B$6:$B$22,$A115,'S4'!$E$6:$E$22,"Ambos")+SUMIFS('S5'!$I$6:$I$20,'S5'!$B$6:$B$20,$A115,'S5'!$E$6:$E$20,"Víctor")+SUMIFS('S5'!$I$6:$I$20,'S5'!$B$6:$B$20,$A115,'S5'!$E$6:$E$20,"Ambos")+SUMIFS('S6'!$I$6:$I$17,'S6'!$B$6:$B$17,$A115,'S6'!$E$6:$E$17,"Víctor")+SUMIFS('S6'!$I$6:$I$17,'S6'!$B$6:$B$17,$A115,'S6'!$E$6:$E$17,"Ambos")+SUMIFS('S7'!$I$6:$I$19,'S7'!$B$6:$B$19,$A115,'S7'!$E$6:$E$19,"Víctor")+SUMIFS('S7'!$I$6:$I$19,'S7'!$B$6:$B$19,$A115,'S7'!$E$6:$E$19,"Ambos")+SUMIFS('S8'!$I$6:$I$23,'S8'!$B$6:$B$23,$A115,'S8'!$E$6:$E$23,"Víctor")+SUMIFS('S8'!$I$6:$I$23,'S8'!$B$6:$B$23,$A115,'S8'!$E$6:$E$23,"Ambos")+SUMIFS('S9'!$I$6:$I$15,'S9'!$B$6:$B$15,$A115,'S9'!$E$6:$E$15,"Víctor")+SUMIFS('S9'!$I$6:$I$15,'S9'!$B$6:$B$15,$A115,'S9'!$E$6:$E$15,"Ambos")+SUMIFS('S10'!$I$6:$I$13,'S10'!$B$6:$B$13,$A115,'S10'!$E$6:$E$13,"Víctor")+SUMIFS('S10'!$I$6:$I$13,'S10'!$B$6:$B$13,$A115,'S10'!$E$6:$E$13,"Ambos")+SUMIFS('Holgura'!$I$6:$I$11,'Holgura'!$B$6:$B$11,$A115,'Holgura'!$E$6:$E$11,"Víctor")+SUMIFS('Holgura'!$I$6:$I$11,'Holgura'!$B$6:$B$11,$A115,'Holgura'!$E$6:$E$11,"Ambos")+SUMIFS('Entrega'!$I$6:$I$9,'Entrega'!$B$6:$B$9,$A115,'Entrega'!$E$6:$E$9,"Víctor")+SUMIFS('Entrega'!$I$6:$I$9,'Entrega'!$B$6:$B$9,$A115,'Entrega'!$E$6:$E$9,"Ambos")+SUMIFS('Defensa'!$I$6:$I$10,'Defensa'!$B$6:$B$10,$A115,'Defensa'!$E$6:$E$10,"Víctor")+SUMIFS('Defensa'!$I$6:$I$10,'Defensa'!$B$6:$B$10,$A115,'Defensa'!$E$6:$E$10,"Ambos")</f>
         <v/>
       </c>
       <c r="E115" s="21">
-        <f>SUMIFS('S1'!$I$6:$I$32,'S1'!$B$6:$B$32,$A115,'S1'!$E$6:$E$32,"Diego")+SUMIFS('S1'!$I$6:$I$32,'S1'!$B$6:$B$32,$A115,'S1'!$E$6:$E$32,"Ambos")+SUMIFS('S2'!$I$6:$I$23,'S2'!$B$6:$B$23,$A115,'S2'!$E$6:$E$23,"Diego")+SUMIFS('S2'!$I$6:$I$23,'S2'!$B$6:$B$23,$A115,'S2'!$E$6:$E$23,"Ambos")+SUMIFS('S3'!$I$6:$I$19,'S3'!$B$6:$B$19,$A115,'S3'!$E$6:$E$19,"Diego")+SUMIFS('S3'!$I$6:$I$19,'S3'!$B$6:$B$19,$A115,'S3'!$E$6:$E$19,"Ambos")+SUMIFS('S4'!$I$6:$I$20,'S4'!$B$6:$B$20,$A115,'S4'!$E$6:$E$20,"Diego")+SUMIFS('S4'!$I$6:$I$20,'S4'!$B$6:$B$20,$A115,'S4'!$E$6:$E$20,"Ambos")+SUMIFS('S5'!$I$6:$I$20,'S5'!$B$6:$B$20,$A115,'S5'!$E$6:$E$20,"Diego")+SUMIFS('S5'!$I$6:$I$20,'S5'!$B$6:$B$20,$A115,'S5'!$E$6:$E$20,"Ambos")+SUMIFS('S6'!$I$6:$I$17,'S6'!$B$6:$B$17,$A115,'S6'!$E$6:$E$17,"Diego")+SUMIFS('S6'!$I$6:$I$17,'S6'!$B$6:$B$17,$A115,'S6'!$E$6:$E$17,"Ambos")+SUMIFS('S7'!$I$6:$I$19,'S7'!$B$6:$B$19,$A115,'S7'!$E$6:$E$19,"Diego")+SUMIFS('S7'!$I$6:$I$19,'S7'!$B$6:$B$19,$A115,'S7'!$E$6:$E$19,"Ambos")+SUMIFS('S8'!$I$6:$I$23,'S8'!$B$6:$B$23,$A115,'S8'!$E$6:$E$23,"Diego")+SUMIFS('S8'!$I$6:$I$23,'S8'!$B$6:$B$23,$A115,'S8'!$E$6:$E$23,"Ambos")+SUMIFS('S9'!$I$6:$I$15,'S9'!$B$6:$B$15,$A115,'S9'!$E$6:$E$15,"Diego")+SUMIFS('S9'!$I$6:$I$15,'S9'!$B$6:$B$15,$A115,'S9'!$E$6:$E$15,"Ambos")+SUMIFS('S10'!$I$6:$I$13,'S10'!$B$6:$B$13,$A115,'S10'!$E$6:$E$13,"Diego")+SUMIFS('S10'!$I$6:$I$13,'S10'!$B$6:$B$13,$A115,'S10'!$E$6:$E$13,"Ambos")+SUMIFS('Holgura'!$I$6:$I$11,'Holgura'!$B$6:$B$11,$A115,'Holgura'!$E$6:$E$11,"Diego")+SUMIFS('Holgura'!$I$6:$I$11,'Holgura'!$B$6:$B$11,$A115,'Holgura'!$E$6:$E$11,"Ambos")+SUMIFS('Entrega'!$I$6:$I$9,'Entrega'!$B$6:$B$9,$A115,'Entrega'!$E$6:$E$9,"Diego")+SUMIFS('Entrega'!$I$6:$I$9,'Entrega'!$B$6:$B$9,$A115,'Entrega'!$E$6:$E$9,"Ambos")+SUMIFS('Defensa'!$I$6:$I$10,'Defensa'!$B$6:$B$10,$A115,'Defensa'!$E$6:$E$10,"Diego")+SUMIFS('Defensa'!$I$6:$I$10,'Defensa'!$B$6:$B$10,$A115,'Defensa'!$E$6:$E$10,"Ambos")</f>
+        <f>SUMIFS('S1'!$I$6:$I$32,'S1'!$B$6:$B$32,$A115,'S1'!$E$6:$E$32,"Diego")+SUMIFS('S1'!$I$6:$I$32,'S1'!$B$6:$B$32,$A115,'S1'!$E$6:$E$32,"Ambos")+SUMIFS('S2'!$I$6:$I$23,'S2'!$B$6:$B$23,$A115,'S2'!$E$6:$E$23,"Diego")+SUMIFS('S2'!$I$6:$I$23,'S2'!$B$6:$B$23,$A115,'S2'!$E$6:$E$23,"Ambos")+SUMIFS('S3'!$I$6:$I$24,'S3'!$B$6:$B$24,$A115,'S3'!$E$6:$E$24,"Diego")+SUMIFS('S3'!$I$6:$I$24,'S3'!$B$6:$B$24,$A115,'S3'!$E$6:$E$24,"Ambos")+SUMIFS('S4'!$I$6:$I$22,'S4'!$B$6:$B$22,$A115,'S4'!$E$6:$E$22,"Diego")+SUMIFS('S4'!$I$6:$I$22,'S4'!$B$6:$B$22,$A115,'S4'!$E$6:$E$22,"Ambos")+SUMIFS('S5'!$I$6:$I$20,'S5'!$B$6:$B$20,$A115,'S5'!$E$6:$E$20,"Diego")+SUMIFS('S5'!$I$6:$I$20,'S5'!$B$6:$B$20,$A115,'S5'!$E$6:$E$20,"Ambos")+SUMIFS('S6'!$I$6:$I$17,'S6'!$B$6:$B$17,$A115,'S6'!$E$6:$E$17,"Diego")+SUMIFS('S6'!$I$6:$I$17,'S6'!$B$6:$B$17,$A115,'S6'!$E$6:$E$17,"Ambos")+SUMIFS('S7'!$I$6:$I$19,'S7'!$B$6:$B$19,$A115,'S7'!$E$6:$E$19,"Diego")+SUMIFS('S7'!$I$6:$I$19,'S7'!$B$6:$B$19,$A115,'S7'!$E$6:$E$19,"Ambos")+SUMIFS('S8'!$I$6:$I$23,'S8'!$B$6:$B$23,$A115,'S8'!$E$6:$E$23,"Diego")+SUMIFS('S8'!$I$6:$I$23,'S8'!$B$6:$B$23,$A115,'S8'!$E$6:$E$23,"Ambos")+SUMIFS('S9'!$I$6:$I$15,'S9'!$B$6:$B$15,$A115,'S9'!$E$6:$E$15,"Diego")+SUMIFS('S9'!$I$6:$I$15,'S9'!$B$6:$B$15,$A115,'S9'!$E$6:$E$15,"Ambos")+SUMIFS('S10'!$I$6:$I$13,'S10'!$B$6:$B$13,$A115,'S10'!$E$6:$E$13,"Diego")+SUMIFS('S10'!$I$6:$I$13,'S10'!$B$6:$B$13,$A115,'S10'!$E$6:$E$13,"Ambos")+SUMIFS('Holgura'!$I$6:$I$11,'Holgura'!$B$6:$B$11,$A115,'Holgura'!$E$6:$E$11,"Diego")+SUMIFS('Holgura'!$I$6:$I$11,'Holgura'!$B$6:$B$11,$A115,'Holgura'!$E$6:$E$11,"Ambos")+SUMIFS('Entrega'!$I$6:$I$9,'Entrega'!$B$6:$B$9,$A115,'Entrega'!$E$6:$E$9,"Diego")+SUMIFS('Entrega'!$I$6:$I$9,'Entrega'!$B$6:$B$9,$A115,'Entrega'!$E$6:$E$9,"Ambos")+SUMIFS('Defensa'!$I$6:$I$10,'Defensa'!$B$6:$B$10,$A115,'Defensa'!$E$6:$E$10,"Diego")+SUMIFS('Defensa'!$I$6:$I$10,'Defensa'!$B$6:$B$10,$A115,'Defensa'!$E$6:$E$10,"Ambos")</f>
         <v/>
       </c>
       <c r="F115" s="21">
-        <f>COUNTIFS('S1'!$B$6:$B$32,$A115,'S1'!$E$6:$E$32,"Víctor")+COUNTIFS('S1'!$B$6:$B$32,$A115,'S1'!$E$6:$E$32,"Ambos")+COUNTIFS('S2'!$B$6:$B$23,$A115,'S2'!$E$6:$E$23,"Víctor")+COUNTIFS('S2'!$B$6:$B$23,$A115,'S2'!$E$6:$E$23,"Ambos")+COUNTIFS('S3'!$B$6:$B$19,$A115,'S3'!$E$6:$E$19,"Víctor")+COUNTIFS('S3'!$B$6:$B$19,$A115,'S3'!$E$6:$E$19,"Ambos")+COUNTIFS('S4'!$B$6:$B$20,$A115,'S4'!$E$6:$E$20,"Víctor")+COUNTIFS('S4'!$B$6:$B$20,$A115,'S4'!$E$6:$E$20,"Ambos")+COUNTIFS('S5'!$B$6:$B$20,$A115,'S5'!$E$6:$E$20,"Víctor")+COUNTIFS('S5'!$B$6:$B$20,$A115,'S5'!$E$6:$E$20,"Ambos")+COUNTIFS('S6'!$B$6:$B$17,$A115,'S6'!$E$6:$E$17,"Víctor")+COUNTIFS('S6'!$B$6:$B$17,$A115,'S6'!$E$6:$E$17,"Ambos")+COUNTIFS('S7'!$B$6:$B$19,$A115,'S7'!$E$6:$E$19,"Víctor")+COUNTIFS('S7'!$B$6:$B$19,$A115,'S7'!$E$6:$E$19,"Ambos")+COUNTIFS('S8'!$B$6:$B$23,$A115,'S8'!$E$6:$E$23,"Víctor")+COUNTIFS('S8'!$B$6:$B$23,$A115,'S8'!$E$6:$E$23,"Ambos")+COUNTIFS('S9'!$B$6:$B$15,$A115,'S9'!$E$6:$E$15,"Víctor")+COUNTIFS('S9'!$B$6:$B$15,$A115,'S9'!$E$6:$E$15,"Ambos")+COUNTIFS('S10'!$B$6:$B$13,$A115,'S10'!$E$6:$E$13,"Víctor")+COUNTIFS('S10'!$B$6:$B$13,$A115,'S10'!$E$6:$E$13,"Ambos")+COUNTIFS('Holgura'!$B$6:$B$11,$A115,'Holgura'!$E$6:$E$11,"Víctor")+COUNTIFS('Holgura'!$B$6:$B$11,$A115,'Holgura'!$E$6:$E$11,"Ambos")+COUNTIFS('Entrega'!$B$6:$B$9,$A115,'Entrega'!$E$6:$E$9,"Víctor")+COUNTIFS('Entrega'!$B$6:$B$9,$A115,'Entrega'!$E$6:$E$9,"Ambos")+COUNTIFS('Defensa'!$B$6:$B$10,$A115,'Defensa'!$E$6:$E$10,"Víctor")+COUNTIFS('Defensa'!$B$6:$B$10,$A115,'Defensa'!$E$6:$E$10,"Ambos")</f>
+        <f>COUNTIFS('S1'!$B$6:$B$32,$A115,'S1'!$E$6:$E$32,"Víctor")+COUNTIFS('S1'!$B$6:$B$32,$A115,'S1'!$E$6:$E$32,"Ambos")+COUNTIFS('S2'!$B$6:$B$23,$A115,'S2'!$E$6:$E$23,"Víctor")+COUNTIFS('S2'!$B$6:$B$23,$A115,'S2'!$E$6:$E$23,"Ambos")+COUNTIFS('S3'!$B$6:$B$24,$A115,'S3'!$E$6:$E$24,"Víctor")+COUNTIFS('S3'!$B$6:$B$24,$A115,'S3'!$E$6:$E$24,"Ambos")+COUNTIFS('S4'!$B$6:$B$22,$A115,'S4'!$E$6:$E$22,"Víctor")+COUNTIFS('S4'!$B$6:$B$22,$A115,'S4'!$E$6:$E$22,"Ambos")+COUNTIFS('S5'!$B$6:$B$20,$A115,'S5'!$E$6:$E$20,"Víctor")+COUNTIFS('S5'!$B$6:$B$20,$A115,'S5'!$E$6:$E$20,"Ambos")+COUNTIFS('S6'!$B$6:$B$17,$A115,'S6'!$E$6:$E$17,"Víctor")+COUNTIFS('S6'!$B$6:$B$17,$A115,'S6'!$E$6:$E$17,"Ambos")+COUNTIFS('S7'!$B$6:$B$19,$A115,'S7'!$E$6:$E$19,"Víctor")+COUNTIFS('S7'!$B$6:$B$19,$A115,'S7'!$E$6:$E$19,"Ambos")+COUNTIFS('S8'!$B$6:$B$23,$A115,'S8'!$E$6:$E$23,"Víctor")+COUNTIFS('S8'!$B$6:$B$23,$A115,'S8'!$E$6:$E$23,"Ambos")+COUNTIFS('S9'!$B$6:$B$15,$A115,'S9'!$E$6:$E$15,"Víctor")+COUNTIFS('S9'!$B$6:$B$15,$A115,'S9'!$E$6:$E$15,"Ambos")+COUNTIFS('S10'!$B$6:$B$13,$A115,'S10'!$E$6:$E$13,"Víctor")+COUNTIFS('S10'!$B$6:$B$13,$A115,'S10'!$E$6:$E$13,"Ambos")+COUNTIFS('Holgura'!$B$6:$B$11,$A115,'Holgura'!$E$6:$E$11,"Víctor")+COUNTIFS('Holgura'!$B$6:$B$11,$A115,'Holgura'!$E$6:$E$11,"Ambos")+COUNTIFS('Entrega'!$B$6:$B$9,$A115,'Entrega'!$E$6:$E$9,"Víctor")+COUNTIFS('Entrega'!$B$6:$B$9,$A115,'Entrega'!$E$6:$E$9,"Ambos")+COUNTIFS('Defensa'!$B$6:$B$10,$A115,'Defensa'!$E$6:$E$10,"Víctor")+COUNTIFS('Defensa'!$B$6:$B$10,$A115,'Defensa'!$E$6:$E$10,"Ambos")</f>
         <v/>
       </c>
       <c r="G115" s="21">
-        <f>COUNTIFS('S1'!$B$6:$B$32,$A115,'S1'!$E$6:$E$32,"Diego")+COUNTIFS('S1'!$B$6:$B$32,$A115,'S1'!$E$6:$E$32,"Ambos")+COUNTIFS('S2'!$B$6:$B$23,$A115,'S2'!$E$6:$E$23,"Diego")+COUNTIFS('S2'!$B$6:$B$23,$A115,'S2'!$E$6:$E$23,"Ambos")+COUNTIFS('S3'!$B$6:$B$19,$A115,'S3'!$E$6:$E$19,"Diego")+COUNTIFS('S3'!$B$6:$B$19,$A115,'S3'!$E$6:$E$19,"Ambos")+COUNTIFS('S4'!$B$6:$B$20,$A115,'S4'!$E$6:$E$20,"Diego")+COUNTIFS('S4'!$B$6:$B$20,$A115,'S4'!$E$6:$E$20,"Ambos")+COUNTIFS('S5'!$B$6:$B$20,$A115,'S5'!$E$6:$E$20,"Diego")+COUNTIFS('S5'!$B$6:$B$20,$A115,'S5'!$E$6:$E$20,"Ambos")+COUNTIFS('S6'!$B$6:$B$17,$A115,'S6'!$E$6:$E$17,"Diego")+COUNTIFS('S6'!$B$6:$B$17,$A115,'S6'!$E$6:$E$17,"Ambos")+COUNTIFS('S7'!$B$6:$B$19,$A115,'S7'!$E$6:$E$19,"Diego")+COUNTIFS('S7'!$B$6:$B$19,$A115,'S7'!$E$6:$E$19,"Ambos")+COUNTIFS('S8'!$B$6:$B$23,$A115,'S8'!$E$6:$E$23,"Diego")+COUNTIFS('S8'!$B$6:$B$23,$A115,'S8'!$E$6:$E$23,"Ambos")+COUNTIFS('S9'!$B$6:$B$15,$A115,'S9'!$E$6:$E$15,"Diego")+COUNTIFS('S9'!$B$6:$B$15,$A115,'S9'!$E$6:$E$15,"Ambos")+COUNTIFS('S10'!$B$6:$B$13,$A115,'S10'!$E$6:$E$13,"Diego")+COUNTIFS('S10'!$B$6:$B$13,$A115,'S10'!$E$6:$E$13,"Ambos")+COUNTIFS('Holgura'!$B$6:$B$11,$A115,'Holgura'!$E$6:$E$11,"Diego")+COUNTIFS('Holgura'!$B$6:$B$11,$A115,'Holgura'!$E$6:$E$11,"Ambos")+COUNTIFS('Entrega'!$B$6:$B$9,$A115,'Entrega'!$E$6:$E$9,"Diego")+COUNTIFS('Entrega'!$B$6:$B$9,$A115,'Entrega'!$E$6:$E$9,"Ambos")+COUNTIFS('Defensa'!$B$6:$B$10,$A115,'Defensa'!$E$6:$E$10,"Diego")+COUNTIFS('Defensa'!$B$6:$B$10,$A115,'Defensa'!$E$6:$E$10,"Ambos")</f>
+        <f>COUNTIFS('S1'!$B$6:$B$32,$A115,'S1'!$E$6:$E$32,"Diego")+COUNTIFS('S1'!$B$6:$B$32,$A115,'S1'!$E$6:$E$32,"Ambos")+COUNTIFS('S2'!$B$6:$B$23,$A115,'S2'!$E$6:$E$23,"Diego")+COUNTIFS('S2'!$B$6:$B$23,$A115,'S2'!$E$6:$E$23,"Ambos")+COUNTIFS('S3'!$B$6:$B$24,$A115,'S3'!$E$6:$E$24,"Diego")+COUNTIFS('S3'!$B$6:$B$24,$A115,'S3'!$E$6:$E$24,"Ambos")+COUNTIFS('S4'!$B$6:$B$22,$A115,'S4'!$E$6:$E$22,"Diego")+COUNTIFS('S4'!$B$6:$B$22,$A115,'S4'!$E$6:$E$22,"Ambos")+COUNTIFS('S5'!$B$6:$B$20,$A115,'S5'!$E$6:$E$20,"Diego")+COUNTIFS('S5'!$B$6:$B$20,$A115,'S5'!$E$6:$E$20,"Ambos")+COUNTIFS('S6'!$B$6:$B$17,$A115,'S6'!$E$6:$E$17,"Diego")+COUNTIFS('S6'!$B$6:$B$17,$A115,'S6'!$E$6:$E$17,"Ambos")+COUNTIFS('S7'!$B$6:$B$19,$A115,'S7'!$E$6:$E$19,"Diego")+COUNTIFS('S7'!$B$6:$B$19,$A115,'S7'!$E$6:$E$19,"Ambos")+COUNTIFS('S8'!$B$6:$B$23,$A115,'S8'!$E$6:$E$23,"Diego")+COUNTIFS('S8'!$B$6:$B$23,$A115,'S8'!$E$6:$E$23,"Ambos")+COUNTIFS('S9'!$B$6:$B$15,$A115,'S9'!$E$6:$E$15,"Diego")+COUNTIFS('S9'!$B$6:$B$15,$A115,'S9'!$E$6:$E$15,"Ambos")+COUNTIFS('S10'!$B$6:$B$13,$A115,'S10'!$E$6:$E$13,"Diego")+COUNTIFS('S10'!$B$6:$B$13,$A115,'S10'!$E$6:$E$13,"Ambos")+COUNTIFS('Holgura'!$B$6:$B$11,$A115,'Holgura'!$E$6:$E$11,"Diego")+COUNTIFS('Holgura'!$B$6:$B$11,$A115,'Holgura'!$E$6:$E$11,"Ambos")+COUNTIFS('Entrega'!$B$6:$B$9,$A115,'Entrega'!$E$6:$E$9,"Diego")+COUNTIFS('Entrega'!$B$6:$B$9,$A115,'Entrega'!$E$6:$E$9,"Ambos")+COUNTIFS('Defensa'!$B$6:$B$10,$A115,'Defensa'!$E$6:$E$10,"Diego")+COUNTIFS('Defensa'!$B$6:$B$10,$A115,'Defensa'!$E$6:$E$10,"Ambos")</f>
         <v/>
       </c>
     </row>
@@ -11899,19 +11920,19 @@
         <v/>
       </c>
       <c r="D116" s="21">
-        <f>SUMIFS('S1'!$I$6:$I$32,'S1'!$B$6:$B$32,$A116,'S1'!$E$6:$E$32,"Víctor")+SUMIFS('S1'!$I$6:$I$32,'S1'!$B$6:$B$32,$A116,'S1'!$E$6:$E$32,"Ambos")+SUMIFS('S2'!$I$6:$I$23,'S2'!$B$6:$B$23,$A116,'S2'!$E$6:$E$23,"Víctor")+SUMIFS('S2'!$I$6:$I$23,'S2'!$B$6:$B$23,$A116,'S2'!$E$6:$E$23,"Ambos")+SUMIFS('S3'!$I$6:$I$19,'S3'!$B$6:$B$19,$A116,'S3'!$E$6:$E$19,"Víctor")+SUMIFS('S3'!$I$6:$I$19,'S3'!$B$6:$B$19,$A116,'S3'!$E$6:$E$19,"Ambos")+SUMIFS('S4'!$I$6:$I$20,'S4'!$B$6:$B$20,$A116,'S4'!$E$6:$E$20,"Víctor")+SUMIFS('S4'!$I$6:$I$20,'S4'!$B$6:$B$20,$A116,'S4'!$E$6:$E$20,"Ambos")+SUMIFS('S5'!$I$6:$I$20,'S5'!$B$6:$B$20,$A116,'S5'!$E$6:$E$20,"Víctor")+SUMIFS('S5'!$I$6:$I$20,'S5'!$B$6:$B$20,$A116,'S5'!$E$6:$E$20,"Ambos")+SUMIFS('S6'!$I$6:$I$17,'S6'!$B$6:$B$17,$A116,'S6'!$E$6:$E$17,"Víctor")+SUMIFS('S6'!$I$6:$I$17,'S6'!$B$6:$B$17,$A116,'S6'!$E$6:$E$17,"Ambos")+SUMIFS('S7'!$I$6:$I$19,'S7'!$B$6:$B$19,$A116,'S7'!$E$6:$E$19,"Víctor")+SUMIFS('S7'!$I$6:$I$19,'S7'!$B$6:$B$19,$A116,'S7'!$E$6:$E$19,"Ambos")+SUMIFS('S8'!$I$6:$I$23,'S8'!$B$6:$B$23,$A116,'S8'!$E$6:$E$23,"Víctor")+SUMIFS('S8'!$I$6:$I$23,'S8'!$B$6:$B$23,$A116,'S8'!$E$6:$E$23,"Ambos")+SUMIFS('S9'!$I$6:$I$15,'S9'!$B$6:$B$15,$A116,'S9'!$E$6:$E$15,"Víctor")+SUMIFS('S9'!$I$6:$I$15,'S9'!$B$6:$B$15,$A116,'S9'!$E$6:$E$15,"Ambos")+SUMIFS('S10'!$I$6:$I$13,'S10'!$B$6:$B$13,$A116,'S10'!$E$6:$E$13,"Víctor")+SUMIFS('S10'!$I$6:$I$13,'S10'!$B$6:$B$13,$A116,'S10'!$E$6:$E$13,"Ambos")+SUMIFS('Holgura'!$I$6:$I$11,'Holgura'!$B$6:$B$11,$A116,'Holgura'!$E$6:$E$11,"Víctor")+SUMIFS('Holgura'!$I$6:$I$11,'Holgura'!$B$6:$B$11,$A116,'Holgura'!$E$6:$E$11,"Ambos")+SUMIFS('Entrega'!$I$6:$I$9,'Entrega'!$B$6:$B$9,$A116,'Entrega'!$E$6:$E$9,"Víctor")+SUMIFS('Entrega'!$I$6:$I$9,'Entrega'!$B$6:$B$9,$A116,'Entrega'!$E$6:$E$9,"Ambos")+SUMIFS('Defensa'!$I$6:$I$10,'Defensa'!$B$6:$B$10,$A116,'Defensa'!$E$6:$E$10,"Víctor")+SUMIFS('Defensa'!$I$6:$I$10,'Defensa'!$B$6:$B$10,$A116,'Defensa'!$E$6:$E$10,"Ambos")</f>
+        <f>SUMIFS('S1'!$I$6:$I$32,'S1'!$B$6:$B$32,$A116,'S1'!$E$6:$E$32,"Víctor")+SUMIFS('S1'!$I$6:$I$32,'S1'!$B$6:$B$32,$A116,'S1'!$E$6:$E$32,"Ambos")+SUMIFS('S2'!$I$6:$I$23,'S2'!$B$6:$B$23,$A116,'S2'!$E$6:$E$23,"Víctor")+SUMIFS('S2'!$I$6:$I$23,'S2'!$B$6:$B$23,$A116,'S2'!$E$6:$E$23,"Ambos")+SUMIFS('S3'!$I$6:$I$24,'S3'!$B$6:$B$24,$A116,'S3'!$E$6:$E$24,"Víctor")+SUMIFS('S3'!$I$6:$I$24,'S3'!$B$6:$B$24,$A116,'S3'!$E$6:$E$24,"Ambos")+SUMIFS('S4'!$I$6:$I$22,'S4'!$B$6:$B$22,$A116,'S4'!$E$6:$E$22,"Víctor")+SUMIFS('S4'!$I$6:$I$22,'S4'!$B$6:$B$22,$A116,'S4'!$E$6:$E$22,"Ambos")+SUMIFS('S5'!$I$6:$I$20,'S5'!$B$6:$B$20,$A116,'S5'!$E$6:$E$20,"Víctor")+SUMIFS('S5'!$I$6:$I$20,'S5'!$B$6:$B$20,$A116,'S5'!$E$6:$E$20,"Ambos")+SUMIFS('S6'!$I$6:$I$17,'S6'!$B$6:$B$17,$A116,'S6'!$E$6:$E$17,"Víctor")+SUMIFS('S6'!$I$6:$I$17,'S6'!$B$6:$B$17,$A116,'S6'!$E$6:$E$17,"Ambos")+SUMIFS('S7'!$I$6:$I$19,'S7'!$B$6:$B$19,$A116,'S7'!$E$6:$E$19,"Víctor")+SUMIFS('S7'!$I$6:$I$19,'S7'!$B$6:$B$19,$A116,'S7'!$E$6:$E$19,"Ambos")+SUMIFS('S8'!$I$6:$I$23,'S8'!$B$6:$B$23,$A116,'S8'!$E$6:$E$23,"Víctor")+SUMIFS('S8'!$I$6:$I$23,'S8'!$B$6:$B$23,$A116,'S8'!$E$6:$E$23,"Ambos")+SUMIFS('S9'!$I$6:$I$15,'S9'!$B$6:$B$15,$A116,'S9'!$E$6:$E$15,"Víctor")+SUMIFS('S9'!$I$6:$I$15,'S9'!$B$6:$B$15,$A116,'S9'!$E$6:$E$15,"Ambos")+SUMIFS('S10'!$I$6:$I$13,'S10'!$B$6:$B$13,$A116,'S10'!$E$6:$E$13,"Víctor")+SUMIFS('S10'!$I$6:$I$13,'S10'!$B$6:$B$13,$A116,'S10'!$E$6:$E$13,"Ambos")+SUMIFS('Holgura'!$I$6:$I$11,'Holgura'!$B$6:$B$11,$A116,'Holgura'!$E$6:$E$11,"Víctor")+SUMIFS('Holgura'!$I$6:$I$11,'Holgura'!$B$6:$B$11,$A116,'Holgura'!$E$6:$E$11,"Ambos")+SUMIFS('Entrega'!$I$6:$I$9,'Entrega'!$B$6:$B$9,$A116,'Entrega'!$E$6:$E$9,"Víctor")+SUMIFS('Entrega'!$I$6:$I$9,'Entrega'!$B$6:$B$9,$A116,'Entrega'!$E$6:$E$9,"Ambos")+SUMIFS('Defensa'!$I$6:$I$10,'Defensa'!$B$6:$B$10,$A116,'Defensa'!$E$6:$E$10,"Víctor")+SUMIFS('Defensa'!$I$6:$I$10,'Defensa'!$B$6:$B$10,$A116,'Defensa'!$E$6:$E$10,"Ambos")</f>
         <v/>
       </c>
       <c r="E116" s="21">
-        <f>SUMIFS('S1'!$I$6:$I$32,'S1'!$B$6:$B$32,$A116,'S1'!$E$6:$E$32,"Diego")+SUMIFS('S1'!$I$6:$I$32,'S1'!$B$6:$B$32,$A116,'S1'!$E$6:$E$32,"Ambos")+SUMIFS('S2'!$I$6:$I$23,'S2'!$B$6:$B$23,$A116,'S2'!$E$6:$E$23,"Diego")+SUMIFS('S2'!$I$6:$I$23,'S2'!$B$6:$B$23,$A116,'S2'!$E$6:$E$23,"Ambos")+SUMIFS('S3'!$I$6:$I$19,'S3'!$B$6:$B$19,$A116,'S3'!$E$6:$E$19,"Diego")+SUMIFS('S3'!$I$6:$I$19,'S3'!$B$6:$B$19,$A116,'S3'!$E$6:$E$19,"Ambos")+SUMIFS('S4'!$I$6:$I$20,'S4'!$B$6:$B$20,$A116,'S4'!$E$6:$E$20,"Diego")+SUMIFS('S4'!$I$6:$I$20,'S4'!$B$6:$B$20,$A116,'S4'!$E$6:$E$20,"Ambos")+SUMIFS('S5'!$I$6:$I$20,'S5'!$B$6:$B$20,$A116,'S5'!$E$6:$E$20,"Diego")+SUMIFS('S5'!$I$6:$I$20,'S5'!$B$6:$B$20,$A116,'S5'!$E$6:$E$20,"Ambos")+SUMIFS('S6'!$I$6:$I$17,'S6'!$B$6:$B$17,$A116,'S6'!$E$6:$E$17,"Diego")+SUMIFS('S6'!$I$6:$I$17,'S6'!$B$6:$B$17,$A116,'S6'!$E$6:$E$17,"Ambos")+SUMIFS('S7'!$I$6:$I$19,'S7'!$B$6:$B$19,$A116,'S7'!$E$6:$E$19,"Diego")+SUMIFS('S7'!$I$6:$I$19,'S7'!$B$6:$B$19,$A116,'S7'!$E$6:$E$19,"Ambos")+SUMIFS('S8'!$I$6:$I$23,'S8'!$B$6:$B$23,$A116,'S8'!$E$6:$E$23,"Diego")+SUMIFS('S8'!$I$6:$I$23,'S8'!$B$6:$B$23,$A116,'S8'!$E$6:$E$23,"Ambos")+SUMIFS('S9'!$I$6:$I$15,'S9'!$B$6:$B$15,$A116,'S9'!$E$6:$E$15,"Diego")+SUMIFS('S9'!$I$6:$I$15,'S9'!$B$6:$B$15,$A116,'S9'!$E$6:$E$15,"Ambos")+SUMIFS('S10'!$I$6:$I$13,'S10'!$B$6:$B$13,$A116,'S10'!$E$6:$E$13,"Diego")+SUMIFS('S10'!$I$6:$I$13,'S10'!$B$6:$B$13,$A116,'S10'!$E$6:$E$13,"Ambos")+SUMIFS('Holgura'!$I$6:$I$11,'Holgura'!$B$6:$B$11,$A116,'Holgura'!$E$6:$E$11,"Diego")+SUMIFS('Holgura'!$I$6:$I$11,'Holgura'!$B$6:$B$11,$A116,'Holgura'!$E$6:$E$11,"Ambos")+SUMIFS('Entrega'!$I$6:$I$9,'Entrega'!$B$6:$B$9,$A116,'Entrega'!$E$6:$E$9,"Diego")+SUMIFS('Entrega'!$I$6:$I$9,'Entrega'!$B$6:$B$9,$A116,'Entrega'!$E$6:$E$9,"Ambos")+SUMIFS('Defensa'!$I$6:$I$10,'Defensa'!$B$6:$B$10,$A116,'Defensa'!$E$6:$E$10,"Diego")+SUMIFS('Defensa'!$I$6:$I$10,'Defensa'!$B$6:$B$10,$A116,'Defensa'!$E$6:$E$10,"Ambos")</f>
+        <f>SUMIFS('S1'!$I$6:$I$32,'S1'!$B$6:$B$32,$A116,'S1'!$E$6:$E$32,"Diego")+SUMIFS('S1'!$I$6:$I$32,'S1'!$B$6:$B$32,$A116,'S1'!$E$6:$E$32,"Ambos")+SUMIFS('S2'!$I$6:$I$23,'S2'!$B$6:$B$23,$A116,'S2'!$E$6:$E$23,"Diego")+SUMIFS('S2'!$I$6:$I$23,'S2'!$B$6:$B$23,$A116,'S2'!$E$6:$E$23,"Ambos")+SUMIFS('S3'!$I$6:$I$24,'S3'!$B$6:$B$24,$A116,'S3'!$E$6:$E$24,"Diego")+SUMIFS('S3'!$I$6:$I$24,'S3'!$B$6:$B$24,$A116,'S3'!$E$6:$E$24,"Ambos")+SUMIFS('S4'!$I$6:$I$22,'S4'!$B$6:$B$22,$A116,'S4'!$E$6:$E$22,"Diego")+SUMIFS('S4'!$I$6:$I$22,'S4'!$B$6:$B$22,$A116,'S4'!$E$6:$E$22,"Ambos")+SUMIFS('S5'!$I$6:$I$20,'S5'!$B$6:$B$20,$A116,'S5'!$E$6:$E$20,"Diego")+SUMIFS('S5'!$I$6:$I$20,'S5'!$B$6:$B$20,$A116,'S5'!$E$6:$E$20,"Ambos")+SUMIFS('S6'!$I$6:$I$17,'S6'!$B$6:$B$17,$A116,'S6'!$E$6:$E$17,"Diego")+SUMIFS('S6'!$I$6:$I$17,'S6'!$B$6:$B$17,$A116,'S6'!$E$6:$E$17,"Ambos")+SUMIFS('S7'!$I$6:$I$19,'S7'!$B$6:$B$19,$A116,'S7'!$E$6:$E$19,"Diego")+SUMIFS('S7'!$I$6:$I$19,'S7'!$B$6:$B$19,$A116,'S7'!$E$6:$E$19,"Ambos")+SUMIFS('S8'!$I$6:$I$23,'S8'!$B$6:$B$23,$A116,'S8'!$E$6:$E$23,"Diego")+SUMIFS('S8'!$I$6:$I$23,'S8'!$B$6:$B$23,$A116,'S8'!$E$6:$E$23,"Ambos")+SUMIFS('S9'!$I$6:$I$15,'S9'!$B$6:$B$15,$A116,'S9'!$E$6:$E$15,"Diego")+SUMIFS('S9'!$I$6:$I$15,'S9'!$B$6:$B$15,$A116,'S9'!$E$6:$E$15,"Ambos")+SUMIFS('S10'!$I$6:$I$13,'S10'!$B$6:$B$13,$A116,'S10'!$E$6:$E$13,"Diego")+SUMIFS('S10'!$I$6:$I$13,'S10'!$B$6:$B$13,$A116,'S10'!$E$6:$E$13,"Ambos")+SUMIFS('Holgura'!$I$6:$I$11,'Holgura'!$B$6:$B$11,$A116,'Holgura'!$E$6:$E$11,"Diego")+SUMIFS('Holgura'!$I$6:$I$11,'Holgura'!$B$6:$B$11,$A116,'Holgura'!$E$6:$E$11,"Ambos")+SUMIFS('Entrega'!$I$6:$I$9,'Entrega'!$B$6:$B$9,$A116,'Entrega'!$E$6:$E$9,"Diego")+SUMIFS('Entrega'!$I$6:$I$9,'Entrega'!$B$6:$B$9,$A116,'Entrega'!$E$6:$E$9,"Ambos")+SUMIFS('Defensa'!$I$6:$I$10,'Defensa'!$B$6:$B$10,$A116,'Defensa'!$E$6:$E$10,"Diego")+SUMIFS('Defensa'!$I$6:$I$10,'Defensa'!$B$6:$B$10,$A116,'Defensa'!$E$6:$E$10,"Ambos")</f>
         <v/>
       </c>
       <c r="F116" s="21">
-        <f>COUNTIFS('S1'!$B$6:$B$32,$A116,'S1'!$E$6:$E$32,"Víctor")+COUNTIFS('S1'!$B$6:$B$32,$A116,'S1'!$E$6:$E$32,"Ambos")+COUNTIFS('S2'!$B$6:$B$23,$A116,'S2'!$E$6:$E$23,"Víctor")+COUNTIFS('S2'!$B$6:$B$23,$A116,'S2'!$E$6:$E$23,"Ambos")+COUNTIFS('S3'!$B$6:$B$19,$A116,'S3'!$E$6:$E$19,"Víctor")+COUNTIFS('S3'!$B$6:$B$19,$A116,'S3'!$E$6:$E$19,"Ambos")+COUNTIFS('S4'!$B$6:$B$20,$A116,'S4'!$E$6:$E$20,"Víctor")+COUNTIFS('S4'!$B$6:$B$20,$A116,'S4'!$E$6:$E$20,"Ambos")+COUNTIFS('S5'!$B$6:$B$20,$A116,'S5'!$E$6:$E$20,"Víctor")+COUNTIFS('S5'!$B$6:$B$20,$A116,'S5'!$E$6:$E$20,"Ambos")+COUNTIFS('S6'!$B$6:$B$17,$A116,'S6'!$E$6:$E$17,"Víctor")+COUNTIFS('S6'!$B$6:$B$17,$A116,'S6'!$E$6:$E$17,"Ambos")+COUNTIFS('S7'!$B$6:$B$19,$A116,'S7'!$E$6:$E$19,"Víctor")+COUNTIFS('S7'!$B$6:$B$19,$A116,'S7'!$E$6:$E$19,"Ambos")+COUNTIFS('S8'!$B$6:$B$23,$A116,'S8'!$E$6:$E$23,"Víctor")+COUNTIFS('S8'!$B$6:$B$23,$A116,'S8'!$E$6:$E$23,"Ambos")+COUNTIFS('S9'!$B$6:$B$15,$A116,'S9'!$E$6:$E$15,"Víctor")+COUNTIFS('S9'!$B$6:$B$15,$A116,'S9'!$E$6:$E$15,"Ambos")+COUNTIFS('S10'!$B$6:$B$13,$A116,'S10'!$E$6:$E$13,"Víctor")+COUNTIFS('S10'!$B$6:$B$13,$A116,'S10'!$E$6:$E$13,"Ambos")+COUNTIFS('Holgura'!$B$6:$B$11,$A116,'Holgura'!$E$6:$E$11,"Víctor")+COUNTIFS('Holgura'!$B$6:$B$11,$A116,'Holgura'!$E$6:$E$11,"Ambos")+COUNTIFS('Entrega'!$B$6:$B$9,$A116,'Entrega'!$E$6:$E$9,"Víctor")+COUNTIFS('Entrega'!$B$6:$B$9,$A116,'Entrega'!$E$6:$E$9,"Ambos")+COUNTIFS('Defensa'!$B$6:$B$10,$A116,'Defensa'!$E$6:$E$10,"Víctor")+COUNTIFS('Defensa'!$B$6:$B$10,$A116,'Defensa'!$E$6:$E$10,"Ambos")</f>
+        <f>COUNTIFS('S1'!$B$6:$B$32,$A116,'S1'!$E$6:$E$32,"Víctor")+COUNTIFS('S1'!$B$6:$B$32,$A116,'S1'!$E$6:$E$32,"Ambos")+COUNTIFS('S2'!$B$6:$B$23,$A116,'S2'!$E$6:$E$23,"Víctor")+COUNTIFS('S2'!$B$6:$B$23,$A116,'S2'!$E$6:$E$23,"Ambos")+COUNTIFS('S3'!$B$6:$B$24,$A116,'S3'!$E$6:$E$24,"Víctor")+COUNTIFS('S3'!$B$6:$B$24,$A116,'S3'!$E$6:$E$24,"Ambos")+COUNTIFS('S4'!$B$6:$B$22,$A116,'S4'!$E$6:$E$22,"Víctor")+COUNTIFS('S4'!$B$6:$B$22,$A116,'S4'!$E$6:$E$22,"Ambos")+COUNTIFS('S5'!$B$6:$B$20,$A116,'S5'!$E$6:$E$20,"Víctor")+COUNTIFS('S5'!$B$6:$B$20,$A116,'S5'!$E$6:$E$20,"Ambos")+COUNTIFS('S6'!$B$6:$B$17,$A116,'S6'!$E$6:$E$17,"Víctor")+COUNTIFS('S6'!$B$6:$B$17,$A116,'S6'!$E$6:$E$17,"Ambos")+COUNTIFS('S7'!$B$6:$B$19,$A116,'S7'!$E$6:$E$19,"Víctor")+COUNTIFS('S7'!$B$6:$B$19,$A116,'S7'!$E$6:$E$19,"Ambos")+COUNTIFS('S8'!$B$6:$B$23,$A116,'S8'!$E$6:$E$23,"Víctor")+COUNTIFS('S8'!$B$6:$B$23,$A116,'S8'!$E$6:$E$23,"Ambos")+COUNTIFS('S9'!$B$6:$B$15,$A116,'S9'!$E$6:$E$15,"Víctor")+COUNTIFS('S9'!$B$6:$B$15,$A116,'S9'!$E$6:$E$15,"Ambos")+COUNTIFS('S10'!$B$6:$B$13,$A116,'S10'!$E$6:$E$13,"Víctor")+COUNTIFS('S10'!$B$6:$B$13,$A116,'S10'!$E$6:$E$13,"Ambos")+COUNTIFS('Holgura'!$B$6:$B$11,$A116,'Holgura'!$E$6:$E$11,"Víctor")+COUNTIFS('Holgura'!$B$6:$B$11,$A116,'Holgura'!$E$6:$E$11,"Ambos")+COUNTIFS('Entrega'!$B$6:$B$9,$A116,'Entrega'!$E$6:$E$9,"Víctor")+COUNTIFS('Entrega'!$B$6:$B$9,$A116,'Entrega'!$E$6:$E$9,"Ambos")+COUNTIFS('Defensa'!$B$6:$B$10,$A116,'Defensa'!$E$6:$E$10,"Víctor")+COUNTIFS('Defensa'!$B$6:$B$10,$A116,'Defensa'!$E$6:$E$10,"Ambos")</f>
         <v/>
       </c>
       <c r="G116" s="21">
-        <f>COUNTIFS('S1'!$B$6:$B$32,$A116,'S1'!$E$6:$E$32,"Diego")+COUNTIFS('S1'!$B$6:$B$32,$A116,'S1'!$E$6:$E$32,"Ambos")+COUNTIFS('S2'!$B$6:$B$23,$A116,'S2'!$E$6:$E$23,"Diego")+COUNTIFS('S2'!$B$6:$B$23,$A116,'S2'!$E$6:$E$23,"Ambos")+COUNTIFS('S3'!$B$6:$B$19,$A116,'S3'!$E$6:$E$19,"Diego")+COUNTIFS('S3'!$B$6:$B$19,$A116,'S3'!$E$6:$E$19,"Ambos")+COUNTIFS('S4'!$B$6:$B$20,$A116,'S4'!$E$6:$E$20,"Diego")+COUNTIFS('S4'!$B$6:$B$20,$A116,'S4'!$E$6:$E$20,"Ambos")+COUNTIFS('S5'!$B$6:$B$20,$A116,'S5'!$E$6:$E$20,"Diego")+COUNTIFS('S5'!$B$6:$B$20,$A116,'S5'!$E$6:$E$20,"Ambos")+COUNTIFS('S6'!$B$6:$B$17,$A116,'S6'!$E$6:$E$17,"Diego")+COUNTIFS('S6'!$B$6:$B$17,$A116,'S6'!$E$6:$E$17,"Ambos")+COUNTIFS('S7'!$B$6:$B$19,$A116,'S7'!$E$6:$E$19,"Diego")+COUNTIFS('S7'!$B$6:$B$19,$A116,'S7'!$E$6:$E$19,"Ambos")+COUNTIFS('S8'!$B$6:$B$23,$A116,'S8'!$E$6:$E$23,"Diego")+COUNTIFS('S8'!$B$6:$B$23,$A116,'S8'!$E$6:$E$23,"Ambos")+COUNTIFS('S9'!$B$6:$B$15,$A116,'S9'!$E$6:$E$15,"Diego")+COUNTIFS('S9'!$B$6:$B$15,$A116,'S9'!$E$6:$E$15,"Ambos")+COUNTIFS('S10'!$B$6:$B$13,$A116,'S10'!$E$6:$E$13,"Diego")+COUNTIFS('S10'!$B$6:$B$13,$A116,'S10'!$E$6:$E$13,"Ambos")+COUNTIFS('Holgura'!$B$6:$B$11,$A116,'Holgura'!$E$6:$E$11,"Diego")+COUNTIFS('Holgura'!$B$6:$B$11,$A116,'Holgura'!$E$6:$E$11,"Ambos")+COUNTIFS('Entrega'!$B$6:$B$9,$A116,'Entrega'!$E$6:$E$9,"Diego")+COUNTIFS('Entrega'!$B$6:$B$9,$A116,'Entrega'!$E$6:$E$9,"Ambos")+COUNTIFS('Defensa'!$B$6:$B$10,$A116,'Defensa'!$E$6:$E$10,"Diego")+COUNTIFS('Defensa'!$B$6:$B$10,$A116,'Defensa'!$E$6:$E$10,"Ambos")</f>
+        <f>COUNTIFS('S1'!$B$6:$B$32,$A116,'S1'!$E$6:$E$32,"Diego")+COUNTIFS('S1'!$B$6:$B$32,$A116,'S1'!$E$6:$E$32,"Ambos")+COUNTIFS('S2'!$B$6:$B$23,$A116,'S2'!$E$6:$E$23,"Diego")+COUNTIFS('S2'!$B$6:$B$23,$A116,'S2'!$E$6:$E$23,"Ambos")+COUNTIFS('S3'!$B$6:$B$24,$A116,'S3'!$E$6:$E$24,"Diego")+COUNTIFS('S3'!$B$6:$B$24,$A116,'S3'!$E$6:$E$24,"Ambos")+COUNTIFS('S4'!$B$6:$B$22,$A116,'S4'!$E$6:$E$22,"Diego")+COUNTIFS('S4'!$B$6:$B$22,$A116,'S4'!$E$6:$E$22,"Ambos")+COUNTIFS('S5'!$B$6:$B$20,$A116,'S5'!$E$6:$E$20,"Diego")+COUNTIFS('S5'!$B$6:$B$20,$A116,'S5'!$E$6:$E$20,"Ambos")+COUNTIFS('S6'!$B$6:$B$17,$A116,'S6'!$E$6:$E$17,"Diego")+COUNTIFS('S6'!$B$6:$B$17,$A116,'S6'!$E$6:$E$17,"Ambos")+COUNTIFS('S7'!$B$6:$B$19,$A116,'S7'!$E$6:$E$19,"Diego")+COUNTIFS('S7'!$B$6:$B$19,$A116,'S7'!$E$6:$E$19,"Ambos")+COUNTIFS('S8'!$B$6:$B$23,$A116,'S8'!$E$6:$E$23,"Diego")+COUNTIFS('S8'!$B$6:$B$23,$A116,'S8'!$E$6:$E$23,"Ambos")+COUNTIFS('S9'!$B$6:$B$15,$A116,'S9'!$E$6:$E$15,"Diego")+COUNTIFS('S9'!$B$6:$B$15,$A116,'S9'!$E$6:$E$15,"Ambos")+COUNTIFS('S10'!$B$6:$B$13,$A116,'S10'!$E$6:$E$13,"Diego")+COUNTIFS('S10'!$B$6:$B$13,$A116,'S10'!$E$6:$E$13,"Ambos")+COUNTIFS('Holgura'!$B$6:$B$11,$A116,'Holgura'!$E$6:$E$11,"Diego")+COUNTIFS('Holgura'!$B$6:$B$11,$A116,'Holgura'!$E$6:$E$11,"Ambos")+COUNTIFS('Entrega'!$B$6:$B$9,$A116,'Entrega'!$E$6:$E$9,"Diego")+COUNTIFS('Entrega'!$B$6:$B$9,$A116,'Entrega'!$E$6:$E$9,"Ambos")+COUNTIFS('Defensa'!$B$6:$B$10,$A116,'Defensa'!$E$6:$E$10,"Diego")+COUNTIFS('Defensa'!$B$6:$B$10,$A116,'Defensa'!$E$6:$E$10,"Ambos")</f>
         <v/>
       </c>
     </row>
@@ -11928,19 +11949,19 @@
         <v/>
       </c>
       <c r="D117" s="21">
-        <f>SUMIFS('S1'!$I$6:$I$32,'S1'!$B$6:$B$32,$A117,'S1'!$E$6:$E$32,"Víctor")+SUMIFS('S1'!$I$6:$I$32,'S1'!$B$6:$B$32,$A117,'S1'!$E$6:$E$32,"Ambos")+SUMIFS('S2'!$I$6:$I$23,'S2'!$B$6:$B$23,$A117,'S2'!$E$6:$E$23,"Víctor")+SUMIFS('S2'!$I$6:$I$23,'S2'!$B$6:$B$23,$A117,'S2'!$E$6:$E$23,"Ambos")+SUMIFS('S3'!$I$6:$I$19,'S3'!$B$6:$B$19,$A117,'S3'!$E$6:$E$19,"Víctor")+SUMIFS('S3'!$I$6:$I$19,'S3'!$B$6:$B$19,$A117,'S3'!$E$6:$E$19,"Ambos")+SUMIFS('S4'!$I$6:$I$20,'S4'!$B$6:$B$20,$A117,'S4'!$E$6:$E$20,"Víctor")+SUMIFS('S4'!$I$6:$I$20,'S4'!$B$6:$B$20,$A117,'S4'!$E$6:$E$20,"Ambos")+SUMIFS('S5'!$I$6:$I$20,'S5'!$B$6:$B$20,$A117,'S5'!$E$6:$E$20,"Víctor")+SUMIFS('S5'!$I$6:$I$20,'S5'!$B$6:$B$20,$A117,'S5'!$E$6:$E$20,"Ambos")+SUMIFS('S6'!$I$6:$I$17,'S6'!$B$6:$B$17,$A117,'S6'!$E$6:$E$17,"Víctor")+SUMIFS('S6'!$I$6:$I$17,'S6'!$B$6:$B$17,$A117,'S6'!$E$6:$E$17,"Ambos")+SUMIFS('S7'!$I$6:$I$19,'S7'!$B$6:$B$19,$A117,'S7'!$E$6:$E$19,"Víctor")+SUMIFS('S7'!$I$6:$I$19,'S7'!$B$6:$B$19,$A117,'S7'!$E$6:$E$19,"Ambos")+SUMIFS('S8'!$I$6:$I$23,'S8'!$B$6:$B$23,$A117,'S8'!$E$6:$E$23,"Víctor")+SUMIFS('S8'!$I$6:$I$23,'S8'!$B$6:$B$23,$A117,'S8'!$E$6:$E$23,"Ambos")+SUMIFS('S9'!$I$6:$I$15,'S9'!$B$6:$B$15,$A117,'S9'!$E$6:$E$15,"Víctor")+SUMIFS('S9'!$I$6:$I$15,'S9'!$B$6:$B$15,$A117,'S9'!$E$6:$E$15,"Ambos")+SUMIFS('S10'!$I$6:$I$13,'S10'!$B$6:$B$13,$A117,'S10'!$E$6:$E$13,"Víctor")+SUMIFS('S10'!$I$6:$I$13,'S10'!$B$6:$B$13,$A117,'S10'!$E$6:$E$13,"Ambos")+SUMIFS('Holgura'!$I$6:$I$11,'Holgura'!$B$6:$B$11,$A117,'Holgura'!$E$6:$E$11,"Víctor")+SUMIFS('Holgura'!$I$6:$I$11,'Holgura'!$B$6:$B$11,$A117,'Holgura'!$E$6:$E$11,"Ambos")+SUMIFS('Entrega'!$I$6:$I$9,'Entrega'!$B$6:$B$9,$A117,'Entrega'!$E$6:$E$9,"Víctor")+SUMIFS('Entrega'!$I$6:$I$9,'Entrega'!$B$6:$B$9,$A117,'Entrega'!$E$6:$E$9,"Ambos")+SUMIFS('Defensa'!$I$6:$I$10,'Defensa'!$B$6:$B$10,$A117,'Defensa'!$E$6:$E$10,"Víctor")+SUMIFS('Defensa'!$I$6:$I$10,'Defensa'!$B$6:$B$10,$A117,'Defensa'!$E$6:$E$10,"Ambos")</f>
+        <f>SUMIFS('S1'!$I$6:$I$32,'S1'!$B$6:$B$32,$A117,'S1'!$E$6:$E$32,"Víctor")+SUMIFS('S1'!$I$6:$I$32,'S1'!$B$6:$B$32,$A117,'S1'!$E$6:$E$32,"Ambos")+SUMIFS('S2'!$I$6:$I$23,'S2'!$B$6:$B$23,$A117,'S2'!$E$6:$E$23,"Víctor")+SUMIFS('S2'!$I$6:$I$23,'S2'!$B$6:$B$23,$A117,'S2'!$E$6:$E$23,"Ambos")+SUMIFS('S3'!$I$6:$I$24,'S3'!$B$6:$B$24,$A117,'S3'!$E$6:$E$24,"Víctor")+SUMIFS('S3'!$I$6:$I$24,'S3'!$B$6:$B$24,$A117,'S3'!$E$6:$E$24,"Ambos")+SUMIFS('S4'!$I$6:$I$22,'S4'!$B$6:$B$22,$A117,'S4'!$E$6:$E$22,"Víctor")+SUMIFS('S4'!$I$6:$I$22,'S4'!$B$6:$B$22,$A117,'S4'!$E$6:$E$22,"Ambos")+SUMIFS('S5'!$I$6:$I$20,'S5'!$B$6:$B$20,$A117,'S5'!$E$6:$E$20,"Víctor")+SUMIFS('S5'!$I$6:$I$20,'S5'!$B$6:$B$20,$A117,'S5'!$E$6:$E$20,"Ambos")+SUMIFS('S6'!$I$6:$I$17,'S6'!$B$6:$B$17,$A117,'S6'!$E$6:$E$17,"Víctor")+SUMIFS('S6'!$I$6:$I$17,'S6'!$B$6:$B$17,$A117,'S6'!$E$6:$E$17,"Ambos")+SUMIFS('S7'!$I$6:$I$19,'S7'!$B$6:$B$19,$A117,'S7'!$E$6:$E$19,"Víctor")+SUMIFS('S7'!$I$6:$I$19,'S7'!$B$6:$B$19,$A117,'S7'!$E$6:$E$19,"Ambos")+SUMIFS('S8'!$I$6:$I$23,'S8'!$B$6:$B$23,$A117,'S8'!$E$6:$E$23,"Víctor")+SUMIFS('S8'!$I$6:$I$23,'S8'!$B$6:$B$23,$A117,'S8'!$E$6:$E$23,"Ambos")+SUMIFS('S9'!$I$6:$I$15,'S9'!$B$6:$B$15,$A117,'S9'!$E$6:$E$15,"Víctor")+SUMIFS('S9'!$I$6:$I$15,'S9'!$B$6:$B$15,$A117,'S9'!$E$6:$E$15,"Ambos")+SUMIFS('S10'!$I$6:$I$13,'S10'!$B$6:$B$13,$A117,'S10'!$E$6:$E$13,"Víctor")+SUMIFS('S10'!$I$6:$I$13,'S10'!$B$6:$B$13,$A117,'S10'!$E$6:$E$13,"Ambos")+SUMIFS('Holgura'!$I$6:$I$11,'Holgura'!$B$6:$B$11,$A117,'Holgura'!$E$6:$E$11,"Víctor")+SUMIFS('Holgura'!$I$6:$I$11,'Holgura'!$B$6:$B$11,$A117,'Holgura'!$E$6:$E$11,"Ambos")+SUMIFS('Entrega'!$I$6:$I$9,'Entrega'!$B$6:$B$9,$A117,'Entrega'!$E$6:$E$9,"Víctor")+SUMIFS('Entrega'!$I$6:$I$9,'Entrega'!$B$6:$B$9,$A117,'Entrega'!$E$6:$E$9,"Ambos")+SUMIFS('Defensa'!$I$6:$I$10,'Defensa'!$B$6:$B$10,$A117,'Defensa'!$E$6:$E$10,"Víctor")+SUMIFS('Defensa'!$I$6:$I$10,'Defensa'!$B$6:$B$10,$A117,'Defensa'!$E$6:$E$10,"Ambos")</f>
         <v/>
       </c>
       <c r="E117" s="21">
-        <f>SUMIFS('S1'!$I$6:$I$32,'S1'!$B$6:$B$32,$A117,'S1'!$E$6:$E$32,"Diego")+SUMIFS('S1'!$I$6:$I$32,'S1'!$B$6:$B$32,$A117,'S1'!$E$6:$E$32,"Ambos")+SUMIFS('S2'!$I$6:$I$23,'S2'!$B$6:$B$23,$A117,'S2'!$E$6:$E$23,"Diego")+SUMIFS('S2'!$I$6:$I$23,'S2'!$B$6:$B$23,$A117,'S2'!$E$6:$E$23,"Ambos")+SUMIFS('S3'!$I$6:$I$19,'S3'!$B$6:$B$19,$A117,'S3'!$E$6:$E$19,"Diego")+SUMIFS('S3'!$I$6:$I$19,'S3'!$B$6:$B$19,$A117,'S3'!$E$6:$E$19,"Ambos")+SUMIFS('S4'!$I$6:$I$20,'S4'!$B$6:$B$20,$A117,'S4'!$E$6:$E$20,"Diego")+SUMIFS('S4'!$I$6:$I$20,'S4'!$B$6:$B$20,$A117,'S4'!$E$6:$E$20,"Ambos")+SUMIFS('S5'!$I$6:$I$20,'S5'!$B$6:$B$20,$A117,'S5'!$E$6:$E$20,"Diego")+SUMIFS('S5'!$I$6:$I$20,'S5'!$B$6:$B$20,$A117,'S5'!$E$6:$E$20,"Ambos")+SUMIFS('S6'!$I$6:$I$17,'S6'!$B$6:$B$17,$A117,'S6'!$E$6:$E$17,"Diego")+SUMIFS('S6'!$I$6:$I$17,'S6'!$B$6:$B$17,$A117,'S6'!$E$6:$E$17,"Ambos")+SUMIFS('S7'!$I$6:$I$19,'S7'!$B$6:$B$19,$A117,'S7'!$E$6:$E$19,"Diego")+SUMIFS('S7'!$I$6:$I$19,'S7'!$B$6:$B$19,$A117,'S7'!$E$6:$E$19,"Ambos")+SUMIFS('S8'!$I$6:$I$23,'S8'!$B$6:$B$23,$A117,'S8'!$E$6:$E$23,"Diego")+SUMIFS('S8'!$I$6:$I$23,'S8'!$B$6:$B$23,$A117,'S8'!$E$6:$E$23,"Ambos")+SUMIFS('S9'!$I$6:$I$15,'S9'!$B$6:$B$15,$A117,'S9'!$E$6:$E$15,"Diego")+SUMIFS('S9'!$I$6:$I$15,'S9'!$B$6:$B$15,$A117,'S9'!$E$6:$E$15,"Ambos")+SUMIFS('S10'!$I$6:$I$13,'S10'!$B$6:$B$13,$A117,'S10'!$E$6:$E$13,"Diego")+SUMIFS('S10'!$I$6:$I$13,'S10'!$B$6:$B$13,$A117,'S10'!$E$6:$E$13,"Ambos")+SUMIFS('Holgura'!$I$6:$I$11,'Holgura'!$B$6:$B$11,$A117,'Holgura'!$E$6:$E$11,"Diego")+SUMIFS('Holgura'!$I$6:$I$11,'Holgura'!$B$6:$B$11,$A117,'Holgura'!$E$6:$E$11,"Ambos")+SUMIFS('Entrega'!$I$6:$I$9,'Entrega'!$B$6:$B$9,$A117,'Entrega'!$E$6:$E$9,"Diego")+SUMIFS('Entrega'!$I$6:$I$9,'Entrega'!$B$6:$B$9,$A117,'Entrega'!$E$6:$E$9,"Ambos")+SUMIFS('Defensa'!$I$6:$I$10,'Defensa'!$B$6:$B$10,$A117,'Defensa'!$E$6:$E$10,"Diego")+SUMIFS('Defensa'!$I$6:$I$10,'Defensa'!$B$6:$B$10,$A117,'Defensa'!$E$6:$E$10,"Ambos")</f>
+        <f>SUMIFS('S1'!$I$6:$I$32,'S1'!$B$6:$B$32,$A117,'S1'!$E$6:$E$32,"Diego")+SUMIFS('S1'!$I$6:$I$32,'S1'!$B$6:$B$32,$A117,'S1'!$E$6:$E$32,"Ambos")+SUMIFS('S2'!$I$6:$I$23,'S2'!$B$6:$B$23,$A117,'S2'!$E$6:$E$23,"Diego")+SUMIFS('S2'!$I$6:$I$23,'S2'!$B$6:$B$23,$A117,'S2'!$E$6:$E$23,"Ambos")+SUMIFS('S3'!$I$6:$I$24,'S3'!$B$6:$B$24,$A117,'S3'!$E$6:$E$24,"Diego")+SUMIFS('S3'!$I$6:$I$24,'S3'!$B$6:$B$24,$A117,'S3'!$E$6:$E$24,"Ambos")+SUMIFS('S4'!$I$6:$I$22,'S4'!$B$6:$B$22,$A117,'S4'!$E$6:$E$22,"Diego")+SUMIFS('S4'!$I$6:$I$22,'S4'!$B$6:$B$22,$A117,'S4'!$E$6:$E$22,"Ambos")+SUMIFS('S5'!$I$6:$I$20,'S5'!$B$6:$B$20,$A117,'S5'!$E$6:$E$20,"Diego")+SUMIFS('S5'!$I$6:$I$20,'S5'!$B$6:$B$20,$A117,'S5'!$E$6:$E$20,"Ambos")+SUMIFS('S6'!$I$6:$I$17,'S6'!$B$6:$B$17,$A117,'S6'!$E$6:$E$17,"Diego")+SUMIFS('S6'!$I$6:$I$17,'S6'!$B$6:$B$17,$A117,'S6'!$E$6:$E$17,"Ambos")+SUMIFS('S7'!$I$6:$I$19,'S7'!$B$6:$B$19,$A117,'S7'!$E$6:$E$19,"Diego")+SUMIFS('S7'!$I$6:$I$19,'S7'!$B$6:$B$19,$A117,'S7'!$E$6:$E$19,"Ambos")+SUMIFS('S8'!$I$6:$I$23,'S8'!$B$6:$B$23,$A117,'S8'!$E$6:$E$23,"Diego")+SUMIFS('S8'!$I$6:$I$23,'S8'!$B$6:$B$23,$A117,'S8'!$E$6:$E$23,"Ambos")+SUMIFS('S9'!$I$6:$I$15,'S9'!$B$6:$B$15,$A117,'S9'!$E$6:$E$15,"Diego")+SUMIFS('S9'!$I$6:$I$15,'S9'!$B$6:$B$15,$A117,'S9'!$E$6:$E$15,"Ambos")+SUMIFS('S10'!$I$6:$I$13,'S10'!$B$6:$B$13,$A117,'S10'!$E$6:$E$13,"Diego")+SUMIFS('S10'!$I$6:$I$13,'S10'!$B$6:$B$13,$A117,'S10'!$E$6:$E$13,"Ambos")+SUMIFS('Holgura'!$I$6:$I$11,'Holgura'!$B$6:$B$11,$A117,'Holgura'!$E$6:$E$11,"Diego")+SUMIFS('Holgura'!$I$6:$I$11,'Holgura'!$B$6:$B$11,$A117,'Holgura'!$E$6:$E$11,"Ambos")+SUMIFS('Entrega'!$I$6:$I$9,'Entrega'!$B$6:$B$9,$A117,'Entrega'!$E$6:$E$9,"Diego")+SUMIFS('Entrega'!$I$6:$I$9,'Entrega'!$B$6:$B$9,$A117,'Entrega'!$E$6:$E$9,"Ambos")+SUMIFS('Defensa'!$I$6:$I$10,'Defensa'!$B$6:$B$10,$A117,'Defensa'!$E$6:$E$10,"Diego")+SUMIFS('Defensa'!$I$6:$I$10,'Defensa'!$B$6:$B$10,$A117,'Defensa'!$E$6:$E$10,"Ambos")</f>
         <v/>
       </c>
       <c r="F117" s="21">
-        <f>COUNTIFS('S1'!$B$6:$B$32,$A117,'S1'!$E$6:$E$32,"Víctor")+COUNTIFS('S1'!$B$6:$B$32,$A117,'S1'!$E$6:$E$32,"Ambos")+COUNTIFS('S2'!$B$6:$B$23,$A117,'S2'!$E$6:$E$23,"Víctor")+COUNTIFS('S2'!$B$6:$B$23,$A117,'S2'!$E$6:$E$23,"Ambos")+COUNTIFS('S3'!$B$6:$B$19,$A117,'S3'!$E$6:$E$19,"Víctor")+COUNTIFS('S3'!$B$6:$B$19,$A117,'S3'!$E$6:$E$19,"Ambos")+COUNTIFS('S4'!$B$6:$B$20,$A117,'S4'!$E$6:$E$20,"Víctor")+COUNTIFS('S4'!$B$6:$B$20,$A117,'S4'!$E$6:$E$20,"Ambos")+COUNTIFS('S5'!$B$6:$B$20,$A117,'S5'!$E$6:$E$20,"Víctor")+COUNTIFS('S5'!$B$6:$B$20,$A117,'S5'!$E$6:$E$20,"Ambos")+COUNTIFS('S6'!$B$6:$B$17,$A117,'S6'!$E$6:$E$17,"Víctor")+COUNTIFS('S6'!$B$6:$B$17,$A117,'S6'!$E$6:$E$17,"Ambos")+COUNTIFS('S7'!$B$6:$B$19,$A117,'S7'!$E$6:$E$19,"Víctor")+COUNTIFS('S7'!$B$6:$B$19,$A117,'S7'!$E$6:$E$19,"Ambos")+COUNTIFS('S8'!$B$6:$B$23,$A117,'S8'!$E$6:$E$23,"Víctor")+COUNTIFS('S8'!$B$6:$B$23,$A117,'S8'!$E$6:$E$23,"Ambos")+COUNTIFS('S9'!$B$6:$B$15,$A117,'S9'!$E$6:$E$15,"Víctor")+COUNTIFS('S9'!$B$6:$B$15,$A117,'S9'!$E$6:$E$15,"Ambos")+COUNTIFS('S10'!$B$6:$B$13,$A117,'S10'!$E$6:$E$13,"Víctor")+COUNTIFS('S10'!$B$6:$B$13,$A117,'S10'!$E$6:$E$13,"Ambos")+COUNTIFS('Holgura'!$B$6:$B$11,$A117,'Holgura'!$E$6:$E$11,"Víctor")+COUNTIFS('Holgura'!$B$6:$B$11,$A117,'Holgura'!$E$6:$E$11,"Ambos")+COUNTIFS('Entrega'!$B$6:$B$9,$A117,'Entrega'!$E$6:$E$9,"Víctor")+COUNTIFS('Entrega'!$B$6:$B$9,$A117,'Entrega'!$E$6:$E$9,"Ambos")+COUNTIFS('Defensa'!$B$6:$B$10,$A117,'Defensa'!$E$6:$E$10,"Víctor")+COUNTIFS('Defensa'!$B$6:$B$10,$A117,'Defensa'!$E$6:$E$10,"Ambos")</f>
+        <f>COUNTIFS('S1'!$B$6:$B$32,$A117,'S1'!$E$6:$E$32,"Víctor")+COUNTIFS('S1'!$B$6:$B$32,$A117,'S1'!$E$6:$E$32,"Ambos")+COUNTIFS('S2'!$B$6:$B$23,$A117,'S2'!$E$6:$E$23,"Víctor")+COUNTIFS('S2'!$B$6:$B$23,$A117,'S2'!$E$6:$E$23,"Ambos")+COUNTIFS('S3'!$B$6:$B$24,$A117,'S3'!$E$6:$E$24,"Víctor")+COUNTIFS('S3'!$B$6:$B$24,$A117,'S3'!$E$6:$E$24,"Ambos")+COUNTIFS('S4'!$B$6:$B$22,$A117,'S4'!$E$6:$E$22,"Víctor")+COUNTIFS('S4'!$B$6:$B$22,$A117,'S4'!$E$6:$E$22,"Ambos")+COUNTIFS('S5'!$B$6:$B$20,$A117,'S5'!$E$6:$E$20,"Víctor")+COUNTIFS('S5'!$B$6:$B$20,$A117,'S5'!$E$6:$E$20,"Ambos")+COUNTIFS('S6'!$B$6:$B$17,$A117,'S6'!$E$6:$E$17,"Víctor")+COUNTIFS('S6'!$B$6:$B$17,$A117,'S6'!$E$6:$E$17,"Ambos")+COUNTIFS('S7'!$B$6:$B$19,$A117,'S7'!$E$6:$E$19,"Víctor")+COUNTIFS('S7'!$B$6:$B$19,$A117,'S7'!$E$6:$E$19,"Ambos")+COUNTIFS('S8'!$B$6:$B$23,$A117,'S8'!$E$6:$E$23,"Víctor")+COUNTIFS('S8'!$B$6:$B$23,$A117,'S8'!$E$6:$E$23,"Ambos")+COUNTIFS('S9'!$B$6:$B$15,$A117,'S9'!$E$6:$E$15,"Víctor")+COUNTIFS('S9'!$B$6:$B$15,$A117,'S9'!$E$6:$E$15,"Ambos")+COUNTIFS('S10'!$B$6:$B$13,$A117,'S10'!$E$6:$E$13,"Víctor")+COUNTIFS('S10'!$B$6:$B$13,$A117,'S10'!$E$6:$E$13,"Ambos")+COUNTIFS('Holgura'!$B$6:$B$11,$A117,'Holgura'!$E$6:$E$11,"Víctor")+COUNTIFS('Holgura'!$B$6:$B$11,$A117,'Holgura'!$E$6:$E$11,"Ambos")+COUNTIFS('Entrega'!$B$6:$B$9,$A117,'Entrega'!$E$6:$E$9,"Víctor")+COUNTIFS('Entrega'!$B$6:$B$9,$A117,'Entrega'!$E$6:$E$9,"Ambos")+COUNTIFS('Defensa'!$B$6:$B$10,$A117,'Defensa'!$E$6:$E$10,"Víctor")+COUNTIFS('Defensa'!$B$6:$B$10,$A117,'Defensa'!$E$6:$E$10,"Ambos")</f>
         <v/>
       </c>
       <c r="G117" s="21">
-        <f>COUNTIFS('S1'!$B$6:$B$32,$A117,'S1'!$E$6:$E$32,"Diego")+COUNTIFS('S1'!$B$6:$B$32,$A117,'S1'!$E$6:$E$32,"Ambos")+COUNTIFS('S2'!$B$6:$B$23,$A117,'S2'!$E$6:$E$23,"Diego")+COUNTIFS('S2'!$B$6:$B$23,$A117,'S2'!$E$6:$E$23,"Ambos")+COUNTIFS('S3'!$B$6:$B$19,$A117,'S3'!$E$6:$E$19,"Diego")+COUNTIFS('S3'!$B$6:$B$19,$A117,'S3'!$E$6:$E$19,"Ambos")+COUNTIFS('S4'!$B$6:$B$20,$A117,'S4'!$E$6:$E$20,"Diego")+COUNTIFS('S4'!$B$6:$B$20,$A117,'S4'!$E$6:$E$20,"Ambos")+COUNTIFS('S5'!$B$6:$B$20,$A117,'S5'!$E$6:$E$20,"Diego")+COUNTIFS('S5'!$B$6:$B$20,$A117,'S5'!$E$6:$E$20,"Ambos")+COUNTIFS('S6'!$B$6:$B$17,$A117,'S6'!$E$6:$E$17,"Diego")+COUNTIFS('S6'!$B$6:$B$17,$A117,'S6'!$E$6:$E$17,"Ambos")+COUNTIFS('S7'!$B$6:$B$19,$A117,'S7'!$E$6:$E$19,"Diego")+COUNTIFS('S7'!$B$6:$B$19,$A117,'S7'!$E$6:$E$19,"Ambos")+COUNTIFS('S8'!$B$6:$B$23,$A117,'S8'!$E$6:$E$23,"Diego")+COUNTIFS('S8'!$B$6:$B$23,$A117,'S8'!$E$6:$E$23,"Ambos")+COUNTIFS('S9'!$B$6:$B$15,$A117,'S9'!$E$6:$E$15,"Diego")+COUNTIFS('S9'!$B$6:$B$15,$A117,'S9'!$E$6:$E$15,"Ambos")+COUNTIFS('S10'!$B$6:$B$13,$A117,'S10'!$E$6:$E$13,"Diego")+COUNTIFS('S10'!$B$6:$B$13,$A117,'S10'!$E$6:$E$13,"Ambos")+COUNTIFS('Holgura'!$B$6:$B$11,$A117,'Holgura'!$E$6:$E$11,"Diego")+COUNTIFS('Holgura'!$B$6:$B$11,$A117,'Holgura'!$E$6:$E$11,"Ambos")+COUNTIFS('Entrega'!$B$6:$B$9,$A117,'Entrega'!$E$6:$E$9,"Diego")+COUNTIFS('Entrega'!$B$6:$B$9,$A117,'Entrega'!$E$6:$E$9,"Ambos")+COUNTIFS('Defensa'!$B$6:$B$10,$A117,'Defensa'!$E$6:$E$10,"Diego")+COUNTIFS('Defensa'!$B$6:$B$10,$A117,'Defensa'!$E$6:$E$10,"Ambos")</f>
+        <f>COUNTIFS('S1'!$B$6:$B$32,$A117,'S1'!$E$6:$E$32,"Diego")+COUNTIFS('S1'!$B$6:$B$32,$A117,'S1'!$E$6:$E$32,"Ambos")+COUNTIFS('S2'!$B$6:$B$23,$A117,'S2'!$E$6:$E$23,"Diego")+COUNTIFS('S2'!$B$6:$B$23,$A117,'S2'!$E$6:$E$23,"Ambos")+COUNTIFS('S3'!$B$6:$B$24,$A117,'S3'!$E$6:$E$24,"Diego")+COUNTIFS('S3'!$B$6:$B$24,$A117,'S3'!$E$6:$E$24,"Ambos")+COUNTIFS('S4'!$B$6:$B$22,$A117,'S4'!$E$6:$E$22,"Diego")+COUNTIFS('S4'!$B$6:$B$22,$A117,'S4'!$E$6:$E$22,"Ambos")+COUNTIFS('S5'!$B$6:$B$20,$A117,'S5'!$E$6:$E$20,"Diego")+COUNTIFS('S5'!$B$6:$B$20,$A117,'S5'!$E$6:$E$20,"Ambos")+COUNTIFS('S6'!$B$6:$B$17,$A117,'S6'!$E$6:$E$17,"Diego")+COUNTIFS('S6'!$B$6:$B$17,$A117,'S6'!$E$6:$E$17,"Ambos")+COUNTIFS('S7'!$B$6:$B$19,$A117,'S7'!$E$6:$E$19,"Diego")+COUNTIFS('S7'!$B$6:$B$19,$A117,'S7'!$E$6:$E$19,"Ambos")+COUNTIFS('S8'!$B$6:$B$23,$A117,'S8'!$E$6:$E$23,"Diego")+COUNTIFS('S8'!$B$6:$B$23,$A117,'S8'!$E$6:$E$23,"Ambos")+COUNTIFS('S9'!$B$6:$B$15,$A117,'S9'!$E$6:$E$15,"Diego")+COUNTIFS('S9'!$B$6:$B$15,$A117,'S9'!$E$6:$E$15,"Ambos")+COUNTIFS('S10'!$B$6:$B$13,$A117,'S10'!$E$6:$E$13,"Diego")+COUNTIFS('S10'!$B$6:$B$13,$A117,'S10'!$E$6:$E$13,"Ambos")+COUNTIFS('Holgura'!$B$6:$B$11,$A117,'Holgura'!$E$6:$E$11,"Diego")+COUNTIFS('Holgura'!$B$6:$B$11,$A117,'Holgura'!$E$6:$E$11,"Ambos")+COUNTIFS('Entrega'!$B$6:$B$9,$A117,'Entrega'!$E$6:$E$9,"Diego")+COUNTIFS('Entrega'!$B$6:$B$9,$A117,'Entrega'!$E$6:$E$9,"Ambos")+COUNTIFS('Defensa'!$B$6:$B$10,$A117,'Defensa'!$E$6:$E$10,"Diego")+COUNTIFS('Defensa'!$B$6:$B$10,$A117,'Defensa'!$E$6:$E$10,"Ambos")</f>
         <v/>
       </c>
     </row>
@@ -11957,19 +11978,19 @@
         <v/>
       </c>
       <c r="D118" s="21">
-        <f>SUMIFS('S1'!$I$6:$I$32,'S1'!$B$6:$B$32,$A118,'S1'!$E$6:$E$32,"Víctor")+SUMIFS('S1'!$I$6:$I$32,'S1'!$B$6:$B$32,$A118,'S1'!$E$6:$E$32,"Ambos")+SUMIFS('S2'!$I$6:$I$23,'S2'!$B$6:$B$23,$A118,'S2'!$E$6:$E$23,"Víctor")+SUMIFS('S2'!$I$6:$I$23,'S2'!$B$6:$B$23,$A118,'S2'!$E$6:$E$23,"Ambos")+SUMIFS('S3'!$I$6:$I$19,'S3'!$B$6:$B$19,$A118,'S3'!$E$6:$E$19,"Víctor")+SUMIFS('S3'!$I$6:$I$19,'S3'!$B$6:$B$19,$A118,'S3'!$E$6:$E$19,"Ambos")+SUMIFS('S4'!$I$6:$I$20,'S4'!$B$6:$B$20,$A118,'S4'!$E$6:$E$20,"Víctor")+SUMIFS('S4'!$I$6:$I$20,'S4'!$B$6:$B$20,$A118,'S4'!$E$6:$E$20,"Ambos")+SUMIFS('S5'!$I$6:$I$20,'S5'!$B$6:$B$20,$A118,'S5'!$E$6:$E$20,"Víctor")+SUMIFS('S5'!$I$6:$I$20,'S5'!$B$6:$B$20,$A118,'S5'!$E$6:$E$20,"Ambos")+SUMIFS('S6'!$I$6:$I$17,'S6'!$B$6:$B$17,$A118,'S6'!$E$6:$E$17,"Víctor")+SUMIFS('S6'!$I$6:$I$17,'S6'!$B$6:$B$17,$A118,'S6'!$E$6:$E$17,"Ambos")+SUMIFS('S7'!$I$6:$I$19,'S7'!$B$6:$B$19,$A118,'S7'!$E$6:$E$19,"Víctor")+SUMIFS('S7'!$I$6:$I$19,'S7'!$B$6:$B$19,$A118,'S7'!$E$6:$E$19,"Ambos")+SUMIFS('S8'!$I$6:$I$23,'S8'!$B$6:$B$23,$A118,'S8'!$E$6:$E$23,"Víctor")+SUMIFS('S8'!$I$6:$I$23,'S8'!$B$6:$B$23,$A118,'S8'!$E$6:$E$23,"Ambos")+SUMIFS('S9'!$I$6:$I$15,'S9'!$B$6:$B$15,$A118,'S9'!$E$6:$E$15,"Víctor")+SUMIFS('S9'!$I$6:$I$15,'S9'!$B$6:$B$15,$A118,'S9'!$E$6:$E$15,"Ambos")+SUMIFS('S10'!$I$6:$I$13,'S10'!$B$6:$B$13,$A118,'S10'!$E$6:$E$13,"Víctor")+SUMIFS('S10'!$I$6:$I$13,'S10'!$B$6:$B$13,$A118,'S10'!$E$6:$E$13,"Ambos")+SUMIFS('Holgura'!$I$6:$I$11,'Holgura'!$B$6:$B$11,$A118,'Holgura'!$E$6:$E$11,"Víctor")+SUMIFS('Holgura'!$I$6:$I$11,'Holgura'!$B$6:$B$11,$A118,'Holgura'!$E$6:$E$11,"Ambos")+SUMIFS('Entrega'!$I$6:$I$9,'Entrega'!$B$6:$B$9,$A118,'Entrega'!$E$6:$E$9,"Víctor")+SUMIFS('Entrega'!$I$6:$I$9,'Entrega'!$B$6:$B$9,$A118,'Entrega'!$E$6:$E$9,"Ambos")+SUMIFS('Defensa'!$I$6:$I$10,'Defensa'!$B$6:$B$10,$A118,'Defensa'!$E$6:$E$10,"Víctor")+SUMIFS('Defensa'!$I$6:$I$10,'Defensa'!$B$6:$B$10,$A118,'Defensa'!$E$6:$E$10,"Ambos")</f>
+        <f>SUMIFS('S1'!$I$6:$I$32,'S1'!$B$6:$B$32,$A118,'S1'!$E$6:$E$32,"Víctor")+SUMIFS('S1'!$I$6:$I$32,'S1'!$B$6:$B$32,$A118,'S1'!$E$6:$E$32,"Ambos")+SUMIFS('S2'!$I$6:$I$23,'S2'!$B$6:$B$23,$A118,'S2'!$E$6:$E$23,"Víctor")+SUMIFS('S2'!$I$6:$I$23,'S2'!$B$6:$B$23,$A118,'S2'!$E$6:$E$23,"Ambos")+SUMIFS('S3'!$I$6:$I$24,'S3'!$B$6:$B$24,$A118,'S3'!$E$6:$E$24,"Víctor")+SUMIFS('S3'!$I$6:$I$24,'S3'!$B$6:$B$24,$A118,'S3'!$E$6:$E$24,"Ambos")+SUMIFS('S4'!$I$6:$I$22,'S4'!$B$6:$B$22,$A118,'S4'!$E$6:$E$22,"Víctor")+SUMIFS('S4'!$I$6:$I$22,'S4'!$B$6:$B$22,$A118,'S4'!$E$6:$E$22,"Ambos")+SUMIFS('S5'!$I$6:$I$20,'S5'!$B$6:$B$20,$A118,'S5'!$E$6:$E$20,"Víctor")+SUMIFS('S5'!$I$6:$I$20,'S5'!$B$6:$B$20,$A118,'S5'!$E$6:$E$20,"Ambos")+SUMIFS('S6'!$I$6:$I$17,'S6'!$B$6:$B$17,$A118,'S6'!$E$6:$E$17,"Víctor")+SUMIFS('S6'!$I$6:$I$17,'S6'!$B$6:$B$17,$A118,'S6'!$E$6:$E$17,"Ambos")+SUMIFS('S7'!$I$6:$I$19,'S7'!$B$6:$B$19,$A118,'S7'!$E$6:$E$19,"Víctor")+SUMIFS('S7'!$I$6:$I$19,'S7'!$B$6:$B$19,$A118,'S7'!$E$6:$E$19,"Ambos")+SUMIFS('S8'!$I$6:$I$23,'S8'!$B$6:$B$23,$A118,'S8'!$E$6:$E$23,"Víctor")+SUMIFS('S8'!$I$6:$I$23,'S8'!$B$6:$B$23,$A118,'S8'!$E$6:$E$23,"Ambos")+SUMIFS('S9'!$I$6:$I$15,'S9'!$B$6:$B$15,$A118,'S9'!$E$6:$E$15,"Víctor")+SUMIFS('S9'!$I$6:$I$15,'S9'!$B$6:$B$15,$A118,'S9'!$E$6:$E$15,"Ambos")+SUMIFS('S10'!$I$6:$I$13,'S10'!$B$6:$B$13,$A118,'S10'!$E$6:$E$13,"Víctor")+SUMIFS('S10'!$I$6:$I$13,'S10'!$B$6:$B$13,$A118,'S10'!$E$6:$E$13,"Ambos")+SUMIFS('Holgura'!$I$6:$I$11,'Holgura'!$B$6:$B$11,$A118,'Holgura'!$E$6:$E$11,"Víctor")+SUMIFS('Holgura'!$I$6:$I$11,'Holgura'!$B$6:$B$11,$A118,'Holgura'!$E$6:$E$11,"Ambos")+SUMIFS('Entrega'!$I$6:$I$9,'Entrega'!$B$6:$B$9,$A118,'Entrega'!$E$6:$E$9,"Víctor")+SUMIFS('Entrega'!$I$6:$I$9,'Entrega'!$B$6:$B$9,$A118,'Entrega'!$E$6:$E$9,"Ambos")+SUMIFS('Defensa'!$I$6:$I$10,'Defensa'!$B$6:$B$10,$A118,'Defensa'!$E$6:$E$10,"Víctor")+SUMIFS('Defensa'!$I$6:$I$10,'Defensa'!$B$6:$B$10,$A118,'Defensa'!$E$6:$E$10,"Ambos")</f>
         <v/>
       </c>
       <c r="E118" s="21">
-        <f>SUMIFS('S1'!$I$6:$I$32,'S1'!$B$6:$B$32,$A118,'S1'!$E$6:$E$32,"Diego")+SUMIFS('S1'!$I$6:$I$32,'S1'!$B$6:$B$32,$A118,'S1'!$E$6:$E$32,"Ambos")+SUMIFS('S2'!$I$6:$I$23,'S2'!$B$6:$B$23,$A118,'S2'!$E$6:$E$23,"Diego")+SUMIFS('S2'!$I$6:$I$23,'S2'!$B$6:$B$23,$A118,'S2'!$E$6:$E$23,"Ambos")+SUMIFS('S3'!$I$6:$I$19,'S3'!$B$6:$B$19,$A118,'S3'!$E$6:$E$19,"Diego")+SUMIFS('S3'!$I$6:$I$19,'S3'!$B$6:$B$19,$A118,'S3'!$E$6:$E$19,"Ambos")+SUMIFS('S4'!$I$6:$I$20,'S4'!$B$6:$B$20,$A118,'S4'!$E$6:$E$20,"Diego")+SUMIFS('S4'!$I$6:$I$20,'S4'!$B$6:$B$20,$A118,'S4'!$E$6:$E$20,"Ambos")+SUMIFS('S5'!$I$6:$I$20,'S5'!$B$6:$B$20,$A118,'S5'!$E$6:$E$20,"Diego")+SUMIFS('S5'!$I$6:$I$20,'S5'!$B$6:$B$20,$A118,'S5'!$E$6:$E$20,"Ambos")+SUMIFS('S6'!$I$6:$I$17,'S6'!$B$6:$B$17,$A118,'S6'!$E$6:$E$17,"Diego")+SUMIFS('S6'!$I$6:$I$17,'S6'!$B$6:$B$17,$A118,'S6'!$E$6:$E$17,"Ambos")+SUMIFS('S7'!$I$6:$I$19,'S7'!$B$6:$B$19,$A118,'S7'!$E$6:$E$19,"Diego")+SUMIFS('S7'!$I$6:$I$19,'S7'!$B$6:$B$19,$A118,'S7'!$E$6:$E$19,"Ambos")+SUMIFS('S8'!$I$6:$I$23,'S8'!$B$6:$B$23,$A118,'S8'!$E$6:$E$23,"Diego")+SUMIFS('S8'!$I$6:$I$23,'S8'!$B$6:$B$23,$A118,'S8'!$E$6:$E$23,"Ambos")+SUMIFS('S9'!$I$6:$I$15,'S9'!$B$6:$B$15,$A118,'S9'!$E$6:$E$15,"Diego")+SUMIFS('S9'!$I$6:$I$15,'S9'!$B$6:$B$15,$A118,'S9'!$E$6:$E$15,"Ambos")+SUMIFS('S10'!$I$6:$I$13,'S10'!$B$6:$B$13,$A118,'S10'!$E$6:$E$13,"Diego")+SUMIFS('S10'!$I$6:$I$13,'S10'!$B$6:$B$13,$A118,'S10'!$E$6:$E$13,"Ambos")+SUMIFS('Holgura'!$I$6:$I$11,'Holgura'!$B$6:$B$11,$A118,'Holgura'!$E$6:$E$11,"Diego")+SUMIFS('Holgura'!$I$6:$I$11,'Holgura'!$B$6:$B$11,$A118,'Holgura'!$E$6:$E$11,"Ambos")+SUMIFS('Entrega'!$I$6:$I$9,'Entrega'!$B$6:$B$9,$A118,'Entrega'!$E$6:$E$9,"Diego")+SUMIFS('Entrega'!$I$6:$I$9,'Entrega'!$B$6:$B$9,$A118,'Entrega'!$E$6:$E$9,"Ambos")+SUMIFS('Defensa'!$I$6:$I$10,'Defensa'!$B$6:$B$10,$A118,'Defensa'!$E$6:$E$10,"Diego")+SUMIFS('Defensa'!$I$6:$I$10,'Defensa'!$B$6:$B$10,$A118,'Defensa'!$E$6:$E$10,"Ambos")</f>
+        <f>SUMIFS('S1'!$I$6:$I$32,'S1'!$B$6:$B$32,$A118,'S1'!$E$6:$E$32,"Diego")+SUMIFS('S1'!$I$6:$I$32,'S1'!$B$6:$B$32,$A118,'S1'!$E$6:$E$32,"Ambos")+SUMIFS('S2'!$I$6:$I$23,'S2'!$B$6:$B$23,$A118,'S2'!$E$6:$E$23,"Diego")+SUMIFS('S2'!$I$6:$I$23,'S2'!$B$6:$B$23,$A118,'S2'!$E$6:$E$23,"Ambos")+SUMIFS('S3'!$I$6:$I$24,'S3'!$B$6:$B$24,$A118,'S3'!$E$6:$E$24,"Diego")+SUMIFS('S3'!$I$6:$I$24,'S3'!$B$6:$B$24,$A118,'S3'!$E$6:$E$24,"Ambos")+SUMIFS('S4'!$I$6:$I$22,'S4'!$B$6:$B$22,$A118,'S4'!$E$6:$E$22,"Diego")+SUMIFS('S4'!$I$6:$I$22,'S4'!$B$6:$B$22,$A118,'S4'!$E$6:$E$22,"Ambos")+SUMIFS('S5'!$I$6:$I$20,'S5'!$B$6:$B$20,$A118,'S5'!$E$6:$E$20,"Diego")+SUMIFS('S5'!$I$6:$I$20,'S5'!$B$6:$B$20,$A118,'S5'!$E$6:$E$20,"Ambos")+SUMIFS('S6'!$I$6:$I$17,'S6'!$B$6:$B$17,$A118,'S6'!$E$6:$E$17,"Diego")+SUMIFS('S6'!$I$6:$I$17,'S6'!$B$6:$B$17,$A118,'S6'!$E$6:$E$17,"Ambos")+SUMIFS('S7'!$I$6:$I$19,'S7'!$B$6:$B$19,$A118,'S7'!$E$6:$E$19,"Diego")+SUMIFS('S7'!$I$6:$I$19,'S7'!$B$6:$B$19,$A118,'S7'!$E$6:$E$19,"Ambos")+SUMIFS('S8'!$I$6:$I$23,'S8'!$B$6:$B$23,$A118,'S8'!$E$6:$E$23,"Diego")+SUMIFS('S8'!$I$6:$I$23,'S8'!$B$6:$B$23,$A118,'S8'!$E$6:$E$23,"Ambos")+SUMIFS('S9'!$I$6:$I$15,'S9'!$B$6:$B$15,$A118,'S9'!$E$6:$E$15,"Diego")+SUMIFS('S9'!$I$6:$I$15,'S9'!$B$6:$B$15,$A118,'S9'!$E$6:$E$15,"Ambos")+SUMIFS('S10'!$I$6:$I$13,'S10'!$B$6:$B$13,$A118,'S10'!$E$6:$E$13,"Diego")+SUMIFS('S10'!$I$6:$I$13,'S10'!$B$6:$B$13,$A118,'S10'!$E$6:$E$13,"Ambos")+SUMIFS('Holgura'!$I$6:$I$11,'Holgura'!$B$6:$B$11,$A118,'Holgura'!$E$6:$E$11,"Diego")+SUMIFS('Holgura'!$I$6:$I$11,'Holgura'!$B$6:$B$11,$A118,'Holgura'!$E$6:$E$11,"Ambos")+SUMIFS('Entrega'!$I$6:$I$9,'Entrega'!$B$6:$B$9,$A118,'Entrega'!$E$6:$E$9,"Diego")+SUMIFS('Entrega'!$I$6:$I$9,'Entrega'!$B$6:$B$9,$A118,'Entrega'!$E$6:$E$9,"Ambos")+SUMIFS('Defensa'!$I$6:$I$10,'Defensa'!$B$6:$B$10,$A118,'Defensa'!$E$6:$E$10,"Diego")+SUMIFS('Defensa'!$I$6:$I$10,'Defensa'!$B$6:$B$10,$A118,'Defensa'!$E$6:$E$10,"Ambos")</f>
         <v/>
       </c>
       <c r="F118" s="21">
-        <f>COUNTIFS('S1'!$B$6:$B$32,$A118,'S1'!$E$6:$E$32,"Víctor")+COUNTIFS('S1'!$B$6:$B$32,$A118,'S1'!$E$6:$E$32,"Ambos")+COUNTIFS('S2'!$B$6:$B$23,$A118,'S2'!$E$6:$E$23,"Víctor")+COUNTIFS('S2'!$B$6:$B$23,$A118,'S2'!$E$6:$E$23,"Ambos")+COUNTIFS('S3'!$B$6:$B$19,$A118,'S3'!$E$6:$E$19,"Víctor")+COUNTIFS('S3'!$B$6:$B$19,$A118,'S3'!$E$6:$E$19,"Ambos")+COUNTIFS('S4'!$B$6:$B$20,$A118,'S4'!$E$6:$E$20,"Víctor")+COUNTIFS('S4'!$B$6:$B$20,$A118,'S4'!$E$6:$E$20,"Ambos")+COUNTIFS('S5'!$B$6:$B$20,$A118,'S5'!$E$6:$E$20,"Víctor")+COUNTIFS('S5'!$B$6:$B$20,$A118,'S5'!$E$6:$E$20,"Ambos")+COUNTIFS('S6'!$B$6:$B$17,$A118,'S6'!$E$6:$E$17,"Víctor")+COUNTIFS('S6'!$B$6:$B$17,$A118,'S6'!$E$6:$E$17,"Ambos")+COUNTIFS('S7'!$B$6:$B$19,$A118,'S7'!$E$6:$E$19,"Víctor")+COUNTIFS('S7'!$B$6:$B$19,$A118,'S7'!$E$6:$E$19,"Ambos")+COUNTIFS('S8'!$B$6:$B$23,$A118,'S8'!$E$6:$E$23,"Víctor")+COUNTIFS('S8'!$B$6:$B$23,$A118,'S8'!$E$6:$E$23,"Ambos")+COUNTIFS('S9'!$B$6:$B$15,$A118,'S9'!$E$6:$E$15,"Víctor")+COUNTIFS('S9'!$B$6:$B$15,$A118,'S9'!$E$6:$E$15,"Ambos")+COUNTIFS('S10'!$B$6:$B$13,$A118,'S10'!$E$6:$E$13,"Víctor")+COUNTIFS('S10'!$B$6:$B$13,$A118,'S10'!$E$6:$E$13,"Ambos")+COUNTIFS('Holgura'!$B$6:$B$11,$A118,'Holgura'!$E$6:$E$11,"Víctor")+COUNTIFS('Holgura'!$B$6:$B$11,$A118,'Holgura'!$E$6:$E$11,"Ambos")+COUNTIFS('Entrega'!$B$6:$B$9,$A118,'Entrega'!$E$6:$E$9,"Víctor")+COUNTIFS('Entrega'!$B$6:$B$9,$A118,'Entrega'!$E$6:$E$9,"Ambos")+COUNTIFS('Defensa'!$B$6:$B$10,$A118,'Defensa'!$E$6:$E$10,"Víctor")+COUNTIFS('Defensa'!$B$6:$B$10,$A118,'Defensa'!$E$6:$E$10,"Ambos")</f>
+        <f>COUNTIFS('S1'!$B$6:$B$32,$A118,'S1'!$E$6:$E$32,"Víctor")+COUNTIFS('S1'!$B$6:$B$32,$A118,'S1'!$E$6:$E$32,"Ambos")+COUNTIFS('S2'!$B$6:$B$23,$A118,'S2'!$E$6:$E$23,"Víctor")+COUNTIFS('S2'!$B$6:$B$23,$A118,'S2'!$E$6:$E$23,"Ambos")+COUNTIFS('S3'!$B$6:$B$24,$A118,'S3'!$E$6:$E$24,"Víctor")+COUNTIFS('S3'!$B$6:$B$24,$A118,'S3'!$E$6:$E$24,"Ambos")+COUNTIFS('S4'!$B$6:$B$22,$A118,'S4'!$E$6:$E$22,"Víctor")+COUNTIFS('S4'!$B$6:$B$22,$A118,'S4'!$E$6:$E$22,"Ambos")+COUNTIFS('S5'!$B$6:$B$20,$A118,'S5'!$E$6:$E$20,"Víctor")+COUNTIFS('S5'!$B$6:$B$20,$A118,'S5'!$E$6:$E$20,"Ambos")+COUNTIFS('S6'!$B$6:$B$17,$A118,'S6'!$E$6:$E$17,"Víctor")+COUNTIFS('S6'!$B$6:$B$17,$A118,'S6'!$E$6:$E$17,"Ambos")+COUNTIFS('S7'!$B$6:$B$19,$A118,'S7'!$E$6:$E$19,"Víctor")+COUNTIFS('S7'!$B$6:$B$19,$A118,'S7'!$E$6:$E$19,"Ambos")+COUNTIFS('S8'!$B$6:$B$23,$A118,'S8'!$E$6:$E$23,"Víctor")+COUNTIFS('S8'!$B$6:$B$23,$A118,'S8'!$E$6:$E$23,"Ambos")+COUNTIFS('S9'!$B$6:$B$15,$A118,'S9'!$E$6:$E$15,"Víctor")+COUNTIFS('S9'!$B$6:$B$15,$A118,'S9'!$E$6:$E$15,"Ambos")+COUNTIFS('S10'!$B$6:$B$13,$A118,'S10'!$E$6:$E$13,"Víctor")+COUNTIFS('S10'!$B$6:$B$13,$A118,'S10'!$E$6:$E$13,"Ambos")+COUNTIFS('Holgura'!$B$6:$B$11,$A118,'Holgura'!$E$6:$E$11,"Víctor")+COUNTIFS('Holgura'!$B$6:$B$11,$A118,'Holgura'!$E$6:$E$11,"Ambos")+COUNTIFS('Entrega'!$B$6:$B$9,$A118,'Entrega'!$E$6:$E$9,"Víctor")+COUNTIFS('Entrega'!$B$6:$B$9,$A118,'Entrega'!$E$6:$E$9,"Ambos")+COUNTIFS('Defensa'!$B$6:$B$10,$A118,'Defensa'!$E$6:$E$10,"Víctor")+COUNTIFS('Defensa'!$B$6:$B$10,$A118,'Defensa'!$E$6:$E$10,"Ambos")</f>
         <v/>
       </c>
       <c r="G118" s="21">
-        <f>COUNTIFS('S1'!$B$6:$B$32,$A118,'S1'!$E$6:$E$32,"Diego")+COUNTIFS('S1'!$B$6:$B$32,$A118,'S1'!$E$6:$E$32,"Ambos")+COUNTIFS('S2'!$B$6:$B$23,$A118,'S2'!$E$6:$E$23,"Diego")+COUNTIFS('S2'!$B$6:$B$23,$A118,'S2'!$E$6:$E$23,"Ambos")+COUNTIFS('S3'!$B$6:$B$19,$A118,'S3'!$E$6:$E$19,"Diego")+COUNTIFS('S3'!$B$6:$B$19,$A118,'S3'!$E$6:$E$19,"Ambos")+COUNTIFS('S4'!$B$6:$B$20,$A118,'S4'!$E$6:$E$20,"Diego")+COUNTIFS('S4'!$B$6:$B$20,$A118,'S4'!$E$6:$E$20,"Ambos")+COUNTIFS('S5'!$B$6:$B$20,$A118,'S5'!$E$6:$E$20,"Diego")+COUNTIFS('S5'!$B$6:$B$20,$A118,'S5'!$E$6:$E$20,"Ambos")+COUNTIFS('S6'!$B$6:$B$17,$A118,'S6'!$E$6:$E$17,"Diego")+COUNTIFS('S6'!$B$6:$B$17,$A118,'S6'!$E$6:$E$17,"Ambos")+COUNTIFS('S7'!$B$6:$B$19,$A118,'S7'!$E$6:$E$19,"Diego")+COUNTIFS('S7'!$B$6:$B$19,$A118,'S7'!$E$6:$E$19,"Ambos")+COUNTIFS('S8'!$B$6:$B$23,$A118,'S8'!$E$6:$E$23,"Diego")+COUNTIFS('S8'!$B$6:$B$23,$A118,'S8'!$E$6:$E$23,"Ambos")+COUNTIFS('S9'!$B$6:$B$15,$A118,'S9'!$E$6:$E$15,"Diego")+COUNTIFS('S9'!$B$6:$B$15,$A118,'S9'!$E$6:$E$15,"Ambos")+COUNTIFS('S10'!$B$6:$B$13,$A118,'S10'!$E$6:$E$13,"Diego")+COUNTIFS('S10'!$B$6:$B$13,$A118,'S10'!$E$6:$E$13,"Ambos")+COUNTIFS('Holgura'!$B$6:$B$11,$A118,'Holgura'!$E$6:$E$11,"Diego")+COUNTIFS('Holgura'!$B$6:$B$11,$A118,'Holgura'!$E$6:$E$11,"Ambos")+COUNTIFS('Entrega'!$B$6:$B$9,$A118,'Entrega'!$E$6:$E$9,"Diego")+COUNTIFS('Entrega'!$B$6:$B$9,$A118,'Entrega'!$E$6:$E$9,"Ambos")+COUNTIFS('Defensa'!$B$6:$B$10,$A118,'Defensa'!$E$6:$E$10,"Diego")+COUNTIFS('Defensa'!$B$6:$B$10,$A118,'Defensa'!$E$6:$E$10,"Ambos")</f>
+        <f>COUNTIFS('S1'!$B$6:$B$32,$A118,'S1'!$E$6:$E$32,"Diego")+COUNTIFS('S1'!$B$6:$B$32,$A118,'S1'!$E$6:$E$32,"Ambos")+COUNTIFS('S2'!$B$6:$B$23,$A118,'S2'!$E$6:$E$23,"Diego")+COUNTIFS('S2'!$B$6:$B$23,$A118,'S2'!$E$6:$E$23,"Ambos")+COUNTIFS('S3'!$B$6:$B$24,$A118,'S3'!$E$6:$E$24,"Diego")+COUNTIFS('S3'!$B$6:$B$24,$A118,'S3'!$E$6:$E$24,"Ambos")+COUNTIFS('S4'!$B$6:$B$22,$A118,'S4'!$E$6:$E$22,"Diego")+COUNTIFS('S4'!$B$6:$B$22,$A118,'S4'!$E$6:$E$22,"Ambos")+COUNTIFS('S5'!$B$6:$B$20,$A118,'S5'!$E$6:$E$20,"Diego")+COUNTIFS('S5'!$B$6:$B$20,$A118,'S5'!$E$6:$E$20,"Ambos")+COUNTIFS('S6'!$B$6:$B$17,$A118,'S6'!$E$6:$E$17,"Diego")+COUNTIFS('S6'!$B$6:$B$17,$A118,'S6'!$E$6:$E$17,"Ambos")+COUNTIFS('S7'!$B$6:$B$19,$A118,'S7'!$E$6:$E$19,"Diego")+COUNTIFS('S7'!$B$6:$B$19,$A118,'S7'!$E$6:$E$19,"Ambos")+COUNTIFS('S8'!$B$6:$B$23,$A118,'S8'!$E$6:$E$23,"Diego")+COUNTIFS('S8'!$B$6:$B$23,$A118,'S8'!$E$6:$E$23,"Ambos")+COUNTIFS('S9'!$B$6:$B$15,$A118,'S9'!$E$6:$E$15,"Diego")+COUNTIFS('S9'!$B$6:$B$15,$A118,'S9'!$E$6:$E$15,"Ambos")+COUNTIFS('S10'!$B$6:$B$13,$A118,'S10'!$E$6:$E$13,"Diego")+COUNTIFS('S10'!$B$6:$B$13,$A118,'S10'!$E$6:$E$13,"Ambos")+COUNTIFS('Holgura'!$B$6:$B$11,$A118,'Holgura'!$E$6:$E$11,"Diego")+COUNTIFS('Holgura'!$B$6:$B$11,$A118,'Holgura'!$E$6:$E$11,"Ambos")+COUNTIFS('Entrega'!$B$6:$B$9,$A118,'Entrega'!$E$6:$E$9,"Diego")+COUNTIFS('Entrega'!$B$6:$B$9,$A118,'Entrega'!$E$6:$E$9,"Ambos")+COUNTIFS('Defensa'!$B$6:$B$10,$A118,'Defensa'!$E$6:$E$10,"Diego")+COUNTIFS('Defensa'!$B$6:$B$10,$A118,'Defensa'!$E$6:$E$10,"Ambos")</f>
         <v/>
       </c>
     </row>
@@ -11986,19 +12007,19 @@
         <v/>
       </c>
       <c r="D119" s="21">
-        <f>SUMIFS('S1'!$I$6:$I$32,'S1'!$B$6:$B$32,$A119,'S1'!$E$6:$E$32,"Víctor")+SUMIFS('S1'!$I$6:$I$32,'S1'!$B$6:$B$32,$A119,'S1'!$E$6:$E$32,"Ambos")+SUMIFS('S2'!$I$6:$I$23,'S2'!$B$6:$B$23,$A119,'S2'!$E$6:$E$23,"Víctor")+SUMIFS('S2'!$I$6:$I$23,'S2'!$B$6:$B$23,$A119,'S2'!$E$6:$E$23,"Ambos")+SUMIFS('S3'!$I$6:$I$19,'S3'!$B$6:$B$19,$A119,'S3'!$E$6:$E$19,"Víctor")+SUMIFS('S3'!$I$6:$I$19,'S3'!$B$6:$B$19,$A119,'S3'!$E$6:$E$19,"Ambos")+SUMIFS('S4'!$I$6:$I$20,'S4'!$B$6:$B$20,$A119,'S4'!$E$6:$E$20,"Víctor")+SUMIFS('S4'!$I$6:$I$20,'S4'!$B$6:$B$20,$A119,'S4'!$E$6:$E$20,"Ambos")+SUMIFS('S5'!$I$6:$I$20,'S5'!$B$6:$B$20,$A119,'S5'!$E$6:$E$20,"Víctor")+SUMIFS('S5'!$I$6:$I$20,'S5'!$B$6:$B$20,$A119,'S5'!$E$6:$E$20,"Ambos")+SUMIFS('S6'!$I$6:$I$17,'S6'!$B$6:$B$17,$A119,'S6'!$E$6:$E$17,"Víctor")+SUMIFS('S6'!$I$6:$I$17,'S6'!$B$6:$B$17,$A119,'S6'!$E$6:$E$17,"Ambos")+SUMIFS('S7'!$I$6:$I$19,'S7'!$B$6:$B$19,$A119,'S7'!$E$6:$E$19,"Víctor")+SUMIFS('S7'!$I$6:$I$19,'S7'!$B$6:$B$19,$A119,'S7'!$E$6:$E$19,"Ambos")+SUMIFS('S8'!$I$6:$I$23,'S8'!$B$6:$B$23,$A119,'S8'!$E$6:$E$23,"Víctor")+SUMIFS('S8'!$I$6:$I$23,'S8'!$B$6:$B$23,$A119,'S8'!$E$6:$E$23,"Ambos")+SUMIFS('S9'!$I$6:$I$15,'S9'!$B$6:$B$15,$A119,'S9'!$E$6:$E$15,"Víctor")+SUMIFS('S9'!$I$6:$I$15,'S9'!$B$6:$B$15,$A119,'S9'!$E$6:$E$15,"Ambos")+SUMIFS('S10'!$I$6:$I$13,'S10'!$B$6:$B$13,$A119,'S10'!$E$6:$E$13,"Víctor")+SUMIFS('S10'!$I$6:$I$13,'S10'!$B$6:$B$13,$A119,'S10'!$E$6:$E$13,"Ambos")+SUMIFS('Holgura'!$I$6:$I$11,'Holgura'!$B$6:$B$11,$A119,'Holgura'!$E$6:$E$11,"Víctor")+SUMIFS('Holgura'!$I$6:$I$11,'Holgura'!$B$6:$B$11,$A119,'Holgura'!$E$6:$E$11,"Ambos")+SUMIFS('Entrega'!$I$6:$I$9,'Entrega'!$B$6:$B$9,$A119,'Entrega'!$E$6:$E$9,"Víctor")+SUMIFS('Entrega'!$I$6:$I$9,'Entrega'!$B$6:$B$9,$A119,'Entrega'!$E$6:$E$9,"Ambos")+SUMIFS('Defensa'!$I$6:$I$10,'Defensa'!$B$6:$B$10,$A119,'Defensa'!$E$6:$E$10,"Víctor")+SUMIFS('Defensa'!$I$6:$I$10,'Defensa'!$B$6:$B$10,$A119,'Defensa'!$E$6:$E$10,"Ambos")</f>
+        <f>SUMIFS('S1'!$I$6:$I$32,'S1'!$B$6:$B$32,$A119,'S1'!$E$6:$E$32,"Víctor")+SUMIFS('S1'!$I$6:$I$32,'S1'!$B$6:$B$32,$A119,'S1'!$E$6:$E$32,"Ambos")+SUMIFS('S2'!$I$6:$I$23,'S2'!$B$6:$B$23,$A119,'S2'!$E$6:$E$23,"Víctor")+SUMIFS('S2'!$I$6:$I$23,'S2'!$B$6:$B$23,$A119,'S2'!$E$6:$E$23,"Ambos")+SUMIFS('S3'!$I$6:$I$24,'S3'!$B$6:$B$24,$A119,'S3'!$E$6:$E$24,"Víctor")+SUMIFS('S3'!$I$6:$I$24,'S3'!$B$6:$B$24,$A119,'S3'!$E$6:$E$24,"Ambos")+SUMIFS('S4'!$I$6:$I$22,'S4'!$B$6:$B$22,$A119,'S4'!$E$6:$E$22,"Víctor")+SUMIFS('S4'!$I$6:$I$22,'S4'!$B$6:$B$22,$A119,'S4'!$E$6:$E$22,"Ambos")+SUMIFS('S5'!$I$6:$I$20,'S5'!$B$6:$B$20,$A119,'S5'!$E$6:$E$20,"Víctor")+SUMIFS('S5'!$I$6:$I$20,'S5'!$B$6:$B$20,$A119,'S5'!$E$6:$E$20,"Ambos")+SUMIFS('S6'!$I$6:$I$17,'S6'!$B$6:$B$17,$A119,'S6'!$E$6:$E$17,"Víctor")+SUMIFS('S6'!$I$6:$I$17,'S6'!$B$6:$B$17,$A119,'S6'!$E$6:$E$17,"Ambos")+SUMIFS('S7'!$I$6:$I$19,'S7'!$B$6:$B$19,$A119,'S7'!$E$6:$E$19,"Víctor")+SUMIFS('S7'!$I$6:$I$19,'S7'!$B$6:$B$19,$A119,'S7'!$E$6:$E$19,"Ambos")+SUMIFS('S8'!$I$6:$I$23,'S8'!$B$6:$B$23,$A119,'S8'!$E$6:$E$23,"Víctor")+SUMIFS('S8'!$I$6:$I$23,'S8'!$B$6:$B$23,$A119,'S8'!$E$6:$E$23,"Ambos")+SUMIFS('S9'!$I$6:$I$15,'S9'!$B$6:$B$15,$A119,'S9'!$E$6:$E$15,"Víctor")+SUMIFS('S9'!$I$6:$I$15,'S9'!$B$6:$B$15,$A119,'S9'!$E$6:$E$15,"Ambos")+SUMIFS('S10'!$I$6:$I$13,'S10'!$B$6:$B$13,$A119,'S10'!$E$6:$E$13,"Víctor")+SUMIFS('S10'!$I$6:$I$13,'S10'!$B$6:$B$13,$A119,'S10'!$E$6:$E$13,"Ambos")+SUMIFS('Holgura'!$I$6:$I$11,'Holgura'!$B$6:$B$11,$A119,'Holgura'!$E$6:$E$11,"Víctor")+SUMIFS('Holgura'!$I$6:$I$11,'Holgura'!$B$6:$B$11,$A119,'Holgura'!$E$6:$E$11,"Ambos")+SUMIFS('Entrega'!$I$6:$I$9,'Entrega'!$B$6:$B$9,$A119,'Entrega'!$E$6:$E$9,"Víctor")+SUMIFS('Entrega'!$I$6:$I$9,'Entrega'!$B$6:$B$9,$A119,'Entrega'!$E$6:$E$9,"Ambos")+SUMIFS('Defensa'!$I$6:$I$10,'Defensa'!$B$6:$B$10,$A119,'Defensa'!$E$6:$E$10,"Víctor")+SUMIFS('Defensa'!$I$6:$I$10,'Defensa'!$B$6:$B$10,$A119,'Defensa'!$E$6:$E$10,"Ambos")</f>
         <v/>
       </c>
       <c r="E119" s="21">
-        <f>SUMIFS('S1'!$I$6:$I$32,'S1'!$B$6:$B$32,$A119,'S1'!$E$6:$E$32,"Diego")+SUMIFS('S1'!$I$6:$I$32,'S1'!$B$6:$B$32,$A119,'S1'!$E$6:$E$32,"Ambos")+SUMIFS('S2'!$I$6:$I$23,'S2'!$B$6:$B$23,$A119,'S2'!$E$6:$E$23,"Diego")+SUMIFS('S2'!$I$6:$I$23,'S2'!$B$6:$B$23,$A119,'S2'!$E$6:$E$23,"Ambos")+SUMIFS('S3'!$I$6:$I$19,'S3'!$B$6:$B$19,$A119,'S3'!$E$6:$E$19,"Diego")+SUMIFS('S3'!$I$6:$I$19,'S3'!$B$6:$B$19,$A119,'S3'!$E$6:$E$19,"Ambos")+SUMIFS('S4'!$I$6:$I$20,'S4'!$B$6:$B$20,$A119,'S4'!$E$6:$E$20,"Diego")+SUMIFS('S4'!$I$6:$I$20,'S4'!$B$6:$B$20,$A119,'S4'!$E$6:$E$20,"Ambos")+SUMIFS('S5'!$I$6:$I$20,'S5'!$B$6:$B$20,$A119,'S5'!$E$6:$E$20,"Diego")+SUMIFS('S5'!$I$6:$I$20,'S5'!$B$6:$B$20,$A119,'S5'!$E$6:$E$20,"Ambos")+SUMIFS('S6'!$I$6:$I$17,'S6'!$B$6:$B$17,$A119,'S6'!$E$6:$E$17,"Diego")+SUMIFS('S6'!$I$6:$I$17,'S6'!$B$6:$B$17,$A119,'S6'!$E$6:$E$17,"Ambos")+SUMIFS('S7'!$I$6:$I$19,'S7'!$B$6:$B$19,$A119,'S7'!$E$6:$E$19,"Diego")+SUMIFS('S7'!$I$6:$I$19,'S7'!$B$6:$B$19,$A119,'S7'!$E$6:$E$19,"Ambos")+SUMIFS('S8'!$I$6:$I$23,'S8'!$B$6:$B$23,$A119,'S8'!$E$6:$E$23,"Diego")+SUMIFS('S8'!$I$6:$I$23,'S8'!$B$6:$B$23,$A119,'S8'!$E$6:$E$23,"Ambos")+SUMIFS('S9'!$I$6:$I$15,'S9'!$B$6:$B$15,$A119,'S9'!$E$6:$E$15,"Diego")+SUMIFS('S9'!$I$6:$I$15,'S9'!$B$6:$B$15,$A119,'S9'!$E$6:$E$15,"Ambos")+SUMIFS('S10'!$I$6:$I$13,'S10'!$B$6:$B$13,$A119,'S10'!$E$6:$E$13,"Diego")+SUMIFS('S10'!$I$6:$I$13,'S10'!$B$6:$B$13,$A119,'S10'!$E$6:$E$13,"Ambos")+SUMIFS('Holgura'!$I$6:$I$11,'Holgura'!$B$6:$B$11,$A119,'Holgura'!$E$6:$E$11,"Diego")+SUMIFS('Holgura'!$I$6:$I$11,'Holgura'!$B$6:$B$11,$A119,'Holgura'!$E$6:$E$11,"Ambos")+SUMIFS('Entrega'!$I$6:$I$9,'Entrega'!$B$6:$B$9,$A119,'Entrega'!$E$6:$E$9,"Diego")+SUMIFS('Entrega'!$I$6:$I$9,'Entrega'!$B$6:$B$9,$A119,'Entrega'!$E$6:$E$9,"Ambos")+SUMIFS('Defensa'!$I$6:$I$10,'Defensa'!$B$6:$B$10,$A119,'Defensa'!$E$6:$E$10,"Diego")+SUMIFS('Defensa'!$I$6:$I$10,'Defensa'!$B$6:$B$10,$A119,'Defensa'!$E$6:$E$10,"Ambos")</f>
+        <f>SUMIFS('S1'!$I$6:$I$32,'S1'!$B$6:$B$32,$A119,'S1'!$E$6:$E$32,"Diego")+SUMIFS('S1'!$I$6:$I$32,'S1'!$B$6:$B$32,$A119,'S1'!$E$6:$E$32,"Ambos")+SUMIFS('S2'!$I$6:$I$23,'S2'!$B$6:$B$23,$A119,'S2'!$E$6:$E$23,"Diego")+SUMIFS('S2'!$I$6:$I$23,'S2'!$B$6:$B$23,$A119,'S2'!$E$6:$E$23,"Ambos")+SUMIFS('S3'!$I$6:$I$24,'S3'!$B$6:$B$24,$A119,'S3'!$E$6:$E$24,"Diego")+SUMIFS('S3'!$I$6:$I$24,'S3'!$B$6:$B$24,$A119,'S3'!$E$6:$E$24,"Ambos")+SUMIFS('S4'!$I$6:$I$22,'S4'!$B$6:$B$22,$A119,'S4'!$E$6:$E$22,"Diego")+SUMIFS('S4'!$I$6:$I$22,'S4'!$B$6:$B$22,$A119,'S4'!$E$6:$E$22,"Ambos")+SUMIFS('S5'!$I$6:$I$20,'S5'!$B$6:$B$20,$A119,'S5'!$E$6:$E$20,"Diego")+SUMIFS('S5'!$I$6:$I$20,'S5'!$B$6:$B$20,$A119,'S5'!$E$6:$E$20,"Ambos")+SUMIFS('S6'!$I$6:$I$17,'S6'!$B$6:$B$17,$A119,'S6'!$E$6:$E$17,"Diego")+SUMIFS('S6'!$I$6:$I$17,'S6'!$B$6:$B$17,$A119,'S6'!$E$6:$E$17,"Ambos")+SUMIFS('S7'!$I$6:$I$19,'S7'!$B$6:$B$19,$A119,'S7'!$E$6:$E$19,"Diego")+SUMIFS('S7'!$I$6:$I$19,'S7'!$B$6:$B$19,$A119,'S7'!$E$6:$E$19,"Ambos")+SUMIFS('S8'!$I$6:$I$23,'S8'!$B$6:$B$23,$A119,'S8'!$E$6:$E$23,"Diego")+SUMIFS('S8'!$I$6:$I$23,'S8'!$B$6:$B$23,$A119,'S8'!$E$6:$E$23,"Ambos")+SUMIFS('S9'!$I$6:$I$15,'S9'!$B$6:$B$15,$A119,'S9'!$E$6:$E$15,"Diego")+SUMIFS('S9'!$I$6:$I$15,'S9'!$B$6:$B$15,$A119,'S9'!$E$6:$E$15,"Ambos")+SUMIFS('S10'!$I$6:$I$13,'S10'!$B$6:$B$13,$A119,'S10'!$E$6:$E$13,"Diego")+SUMIFS('S10'!$I$6:$I$13,'S10'!$B$6:$B$13,$A119,'S10'!$E$6:$E$13,"Ambos")+SUMIFS('Holgura'!$I$6:$I$11,'Holgura'!$B$6:$B$11,$A119,'Holgura'!$E$6:$E$11,"Diego")+SUMIFS('Holgura'!$I$6:$I$11,'Holgura'!$B$6:$B$11,$A119,'Holgura'!$E$6:$E$11,"Ambos")+SUMIFS('Entrega'!$I$6:$I$9,'Entrega'!$B$6:$B$9,$A119,'Entrega'!$E$6:$E$9,"Diego")+SUMIFS('Entrega'!$I$6:$I$9,'Entrega'!$B$6:$B$9,$A119,'Entrega'!$E$6:$E$9,"Ambos")+SUMIFS('Defensa'!$I$6:$I$10,'Defensa'!$B$6:$B$10,$A119,'Defensa'!$E$6:$E$10,"Diego")+SUMIFS('Defensa'!$I$6:$I$10,'Defensa'!$B$6:$B$10,$A119,'Defensa'!$E$6:$E$10,"Ambos")</f>
         <v/>
       </c>
       <c r="F119" s="21">
-        <f>COUNTIFS('S1'!$B$6:$B$32,$A119,'S1'!$E$6:$E$32,"Víctor")+COUNTIFS('S1'!$B$6:$B$32,$A119,'S1'!$E$6:$E$32,"Ambos")+COUNTIFS('S2'!$B$6:$B$23,$A119,'S2'!$E$6:$E$23,"Víctor")+COUNTIFS('S2'!$B$6:$B$23,$A119,'S2'!$E$6:$E$23,"Ambos")+COUNTIFS('S3'!$B$6:$B$19,$A119,'S3'!$E$6:$E$19,"Víctor")+COUNTIFS('S3'!$B$6:$B$19,$A119,'S3'!$E$6:$E$19,"Ambos")+COUNTIFS('S4'!$B$6:$B$20,$A119,'S4'!$E$6:$E$20,"Víctor")+COUNTIFS('S4'!$B$6:$B$20,$A119,'S4'!$E$6:$E$20,"Ambos")+COUNTIFS('S5'!$B$6:$B$20,$A119,'S5'!$E$6:$E$20,"Víctor")+COUNTIFS('S5'!$B$6:$B$20,$A119,'S5'!$E$6:$E$20,"Ambos")+COUNTIFS('S6'!$B$6:$B$17,$A119,'S6'!$E$6:$E$17,"Víctor")+COUNTIFS('S6'!$B$6:$B$17,$A119,'S6'!$E$6:$E$17,"Ambos")+COUNTIFS('S7'!$B$6:$B$19,$A119,'S7'!$E$6:$E$19,"Víctor")+COUNTIFS('S7'!$B$6:$B$19,$A119,'S7'!$E$6:$E$19,"Ambos")+COUNTIFS('S8'!$B$6:$B$23,$A119,'S8'!$E$6:$E$23,"Víctor")+COUNTIFS('S8'!$B$6:$B$23,$A119,'S8'!$E$6:$E$23,"Ambos")+COUNTIFS('S9'!$B$6:$B$15,$A119,'S9'!$E$6:$E$15,"Víctor")+COUNTIFS('S9'!$B$6:$B$15,$A119,'S9'!$E$6:$E$15,"Ambos")+COUNTIFS('S10'!$B$6:$B$13,$A119,'S10'!$E$6:$E$13,"Víctor")+COUNTIFS('S10'!$B$6:$B$13,$A119,'S10'!$E$6:$E$13,"Ambos")+COUNTIFS('Holgura'!$B$6:$B$11,$A119,'Holgura'!$E$6:$E$11,"Víctor")+COUNTIFS('Holgura'!$B$6:$B$11,$A119,'Holgura'!$E$6:$E$11,"Ambos")+COUNTIFS('Entrega'!$B$6:$B$9,$A119,'Entrega'!$E$6:$E$9,"Víctor")+COUNTIFS('Entrega'!$B$6:$B$9,$A119,'Entrega'!$E$6:$E$9,"Ambos")+COUNTIFS('Defensa'!$B$6:$B$10,$A119,'Defensa'!$E$6:$E$10,"Víctor")+COUNTIFS('Defensa'!$B$6:$B$10,$A119,'Defensa'!$E$6:$E$10,"Ambos")</f>
+        <f>COUNTIFS('S1'!$B$6:$B$32,$A119,'S1'!$E$6:$E$32,"Víctor")+COUNTIFS('S1'!$B$6:$B$32,$A119,'S1'!$E$6:$E$32,"Ambos")+COUNTIFS('S2'!$B$6:$B$23,$A119,'S2'!$E$6:$E$23,"Víctor")+COUNTIFS('S2'!$B$6:$B$23,$A119,'S2'!$E$6:$E$23,"Ambos")+COUNTIFS('S3'!$B$6:$B$24,$A119,'S3'!$E$6:$E$24,"Víctor")+COUNTIFS('S3'!$B$6:$B$24,$A119,'S3'!$E$6:$E$24,"Ambos")+COUNTIFS('S4'!$B$6:$B$22,$A119,'S4'!$E$6:$E$22,"Víctor")+COUNTIFS('S4'!$B$6:$B$22,$A119,'S4'!$E$6:$E$22,"Ambos")+COUNTIFS('S5'!$B$6:$B$20,$A119,'S5'!$E$6:$E$20,"Víctor")+COUNTIFS('S5'!$B$6:$B$20,$A119,'S5'!$E$6:$E$20,"Ambos")+COUNTIFS('S6'!$B$6:$B$17,$A119,'S6'!$E$6:$E$17,"Víctor")+COUNTIFS('S6'!$B$6:$B$17,$A119,'S6'!$E$6:$E$17,"Ambos")+COUNTIFS('S7'!$B$6:$B$19,$A119,'S7'!$E$6:$E$19,"Víctor")+COUNTIFS('S7'!$B$6:$B$19,$A119,'S7'!$E$6:$E$19,"Ambos")+COUNTIFS('S8'!$B$6:$B$23,$A119,'S8'!$E$6:$E$23,"Víctor")+COUNTIFS('S8'!$B$6:$B$23,$A119,'S8'!$E$6:$E$23,"Ambos")+COUNTIFS('S9'!$B$6:$B$15,$A119,'S9'!$E$6:$E$15,"Víctor")+COUNTIFS('S9'!$B$6:$B$15,$A119,'S9'!$E$6:$E$15,"Ambos")+COUNTIFS('S10'!$B$6:$B$13,$A119,'S10'!$E$6:$E$13,"Víctor")+COUNTIFS('S10'!$B$6:$B$13,$A119,'S10'!$E$6:$E$13,"Ambos")+COUNTIFS('Holgura'!$B$6:$B$11,$A119,'Holgura'!$E$6:$E$11,"Víctor")+COUNTIFS('Holgura'!$B$6:$B$11,$A119,'Holgura'!$E$6:$E$11,"Ambos")+COUNTIFS('Entrega'!$B$6:$B$9,$A119,'Entrega'!$E$6:$E$9,"Víctor")+COUNTIFS('Entrega'!$B$6:$B$9,$A119,'Entrega'!$E$6:$E$9,"Ambos")+COUNTIFS('Defensa'!$B$6:$B$10,$A119,'Defensa'!$E$6:$E$10,"Víctor")+COUNTIFS('Defensa'!$B$6:$B$10,$A119,'Defensa'!$E$6:$E$10,"Ambos")</f>
         <v/>
       </c>
       <c r="G119" s="21">
-        <f>COUNTIFS('S1'!$B$6:$B$32,$A119,'S1'!$E$6:$E$32,"Diego")+COUNTIFS('S1'!$B$6:$B$32,$A119,'S1'!$E$6:$E$32,"Ambos")+COUNTIFS('S2'!$B$6:$B$23,$A119,'S2'!$E$6:$E$23,"Diego")+COUNTIFS('S2'!$B$6:$B$23,$A119,'S2'!$E$6:$E$23,"Ambos")+COUNTIFS('S3'!$B$6:$B$19,$A119,'S3'!$E$6:$E$19,"Diego")+COUNTIFS('S3'!$B$6:$B$19,$A119,'S3'!$E$6:$E$19,"Ambos")+COUNTIFS('S4'!$B$6:$B$20,$A119,'S4'!$E$6:$E$20,"Diego")+COUNTIFS('S4'!$B$6:$B$20,$A119,'S4'!$E$6:$E$20,"Ambos")+COUNTIFS('S5'!$B$6:$B$20,$A119,'S5'!$E$6:$E$20,"Diego")+COUNTIFS('S5'!$B$6:$B$20,$A119,'S5'!$E$6:$E$20,"Ambos")+COUNTIFS('S6'!$B$6:$B$17,$A119,'S6'!$E$6:$E$17,"Diego")+COUNTIFS('S6'!$B$6:$B$17,$A119,'S6'!$E$6:$E$17,"Ambos")+COUNTIFS('S7'!$B$6:$B$19,$A119,'S7'!$E$6:$E$19,"Diego")+COUNTIFS('S7'!$B$6:$B$19,$A119,'S7'!$E$6:$E$19,"Ambos")+COUNTIFS('S8'!$B$6:$B$23,$A119,'S8'!$E$6:$E$23,"Diego")+COUNTIFS('S8'!$B$6:$B$23,$A119,'S8'!$E$6:$E$23,"Ambos")+COUNTIFS('S9'!$B$6:$B$15,$A119,'S9'!$E$6:$E$15,"Diego")+COUNTIFS('S9'!$B$6:$B$15,$A119,'S9'!$E$6:$E$15,"Ambos")+COUNTIFS('S10'!$B$6:$B$13,$A119,'S10'!$E$6:$E$13,"Diego")+COUNTIFS('S10'!$B$6:$B$13,$A119,'S10'!$E$6:$E$13,"Ambos")+COUNTIFS('Holgura'!$B$6:$B$11,$A119,'Holgura'!$E$6:$E$11,"Diego")+COUNTIFS('Holgura'!$B$6:$B$11,$A119,'Holgura'!$E$6:$E$11,"Ambos")+COUNTIFS('Entrega'!$B$6:$B$9,$A119,'Entrega'!$E$6:$E$9,"Diego")+COUNTIFS('Entrega'!$B$6:$B$9,$A119,'Entrega'!$E$6:$E$9,"Ambos")+COUNTIFS('Defensa'!$B$6:$B$10,$A119,'Defensa'!$E$6:$E$10,"Diego")+COUNTIFS('Defensa'!$B$6:$B$10,$A119,'Defensa'!$E$6:$E$10,"Ambos")</f>
+        <f>COUNTIFS('S1'!$B$6:$B$32,$A119,'S1'!$E$6:$E$32,"Diego")+COUNTIFS('S1'!$B$6:$B$32,$A119,'S1'!$E$6:$E$32,"Ambos")+COUNTIFS('S2'!$B$6:$B$23,$A119,'S2'!$E$6:$E$23,"Diego")+COUNTIFS('S2'!$B$6:$B$23,$A119,'S2'!$E$6:$E$23,"Ambos")+COUNTIFS('S3'!$B$6:$B$24,$A119,'S3'!$E$6:$E$24,"Diego")+COUNTIFS('S3'!$B$6:$B$24,$A119,'S3'!$E$6:$E$24,"Ambos")+COUNTIFS('S4'!$B$6:$B$22,$A119,'S4'!$E$6:$E$22,"Diego")+COUNTIFS('S4'!$B$6:$B$22,$A119,'S4'!$E$6:$E$22,"Ambos")+COUNTIFS('S5'!$B$6:$B$20,$A119,'S5'!$E$6:$E$20,"Diego")+COUNTIFS('S5'!$B$6:$B$20,$A119,'S5'!$E$6:$E$20,"Ambos")+COUNTIFS('S6'!$B$6:$B$17,$A119,'S6'!$E$6:$E$17,"Diego")+COUNTIFS('S6'!$B$6:$B$17,$A119,'S6'!$E$6:$E$17,"Ambos")+COUNTIFS('S7'!$B$6:$B$19,$A119,'S7'!$E$6:$E$19,"Diego")+COUNTIFS('S7'!$B$6:$B$19,$A119,'S7'!$E$6:$E$19,"Ambos")+COUNTIFS('S8'!$B$6:$B$23,$A119,'S8'!$E$6:$E$23,"Diego")+COUNTIFS('S8'!$B$6:$B$23,$A119,'S8'!$E$6:$E$23,"Ambos")+COUNTIFS('S9'!$B$6:$B$15,$A119,'S9'!$E$6:$E$15,"Diego")+COUNTIFS('S9'!$B$6:$B$15,$A119,'S9'!$E$6:$E$15,"Ambos")+COUNTIFS('S10'!$B$6:$B$13,$A119,'S10'!$E$6:$E$13,"Diego")+COUNTIFS('S10'!$B$6:$B$13,$A119,'S10'!$E$6:$E$13,"Ambos")+COUNTIFS('Holgura'!$B$6:$B$11,$A119,'Holgura'!$E$6:$E$11,"Diego")+COUNTIFS('Holgura'!$B$6:$B$11,$A119,'Holgura'!$E$6:$E$11,"Ambos")+COUNTIFS('Entrega'!$B$6:$B$9,$A119,'Entrega'!$E$6:$E$9,"Diego")+COUNTIFS('Entrega'!$B$6:$B$9,$A119,'Entrega'!$E$6:$E$9,"Ambos")+COUNTIFS('Defensa'!$B$6:$B$10,$A119,'Defensa'!$E$6:$E$10,"Diego")+COUNTIFS('Defensa'!$B$6:$B$10,$A119,'Defensa'!$E$6:$E$10,"Ambos")</f>
         <v/>
       </c>
     </row>
@@ -12015,19 +12036,19 @@
         <v/>
       </c>
       <c r="D120" s="21">
-        <f>SUMIFS('S1'!$I$6:$I$32,'S1'!$B$6:$B$32,$A120,'S1'!$E$6:$E$32,"Víctor")+SUMIFS('S1'!$I$6:$I$32,'S1'!$B$6:$B$32,$A120,'S1'!$E$6:$E$32,"Ambos")+SUMIFS('S2'!$I$6:$I$23,'S2'!$B$6:$B$23,$A120,'S2'!$E$6:$E$23,"Víctor")+SUMIFS('S2'!$I$6:$I$23,'S2'!$B$6:$B$23,$A120,'S2'!$E$6:$E$23,"Ambos")+SUMIFS('S3'!$I$6:$I$19,'S3'!$B$6:$B$19,$A120,'S3'!$E$6:$E$19,"Víctor")+SUMIFS('S3'!$I$6:$I$19,'S3'!$B$6:$B$19,$A120,'S3'!$E$6:$E$19,"Ambos")+SUMIFS('S4'!$I$6:$I$20,'S4'!$B$6:$B$20,$A120,'S4'!$E$6:$E$20,"Víctor")+SUMIFS('S4'!$I$6:$I$20,'S4'!$B$6:$B$20,$A120,'S4'!$E$6:$E$20,"Ambos")+SUMIFS('S5'!$I$6:$I$20,'S5'!$B$6:$B$20,$A120,'S5'!$E$6:$E$20,"Víctor")+SUMIFS('S5'!$I$6:$I$20,'S5'!$B$6:$B$20,$A120,'S5'!$E$6:$E$20,"Ambos")+SUMIFS('S6'!$I$6:$I$17,'S6'!$B$6:$B$17,$A120,'S6'!$E$6:$E$17,"Víctor")+SUMIFS('S6'!$I$6:$I$17,'S6'!$B$6:$B$17,$A120,'S6'!$E$6:$E$17,"Ambos")+SUMIFS('S7'!$I$6:$I$19,'S7'!$B$6:$B$19,$A120,'S7'!$E$6:$E$19,"Víctor")+SUMIFS('S7'!$I$6:$I$19,'S7'!$B$6:$B$19,$A120,'S7'!$E$6:$E$19,"Ambos")+SUMIFS('S8'!$I$6:$I$23,'S8'!$B$6:$B$23,$A120,'S8'!$E$6:$E$23,"Víctor")+SUMIFS('S8'!$I$6:$I$23,'S8'!$B$6:$B$23,$A120,'S8'!$E$6:$E$23,"Ambos")+SUMIFS('S9'!$I$6:$I$15,'S9'!$B$6:$B$15,$A120,'S9'!$E$6:$E$15,"Víctor")+SUMIFS('S9'!$I$6:$I$15,'S9'!$B$6:$B$15,$A120,'S9'!$E$6:$E$15,"Ambos")+SUMIFS('S10'!$I$6:$I$13,'S10'!$B$6:$B$13,$A120,'S10'!$E$6:$E$13,"Víctor")+SUMIFS('S10'!$I$6:$I$13,'S10'!$B$6:$B$13,$A120,'S10'!$E$6:$E$13,"Ambos")+SUMIFS('Holgura'!$I$6:$I$11,'Holgura'!$B$6:$B$11,$A120,'Holgura'!$E$6:$E$11,"Víctor")+SUMIFS('Holgura'!$I$6:$I$11,'Holgura'!$B$6:$B$11,$A120,'Holgura'!$E$6:$E$11,"Ambos")+SUMIFS('Entrega'!$I$6:$I$9,'Entrega'!$B$6:$B$9,$A120,'Entrega'!$E$6:$E$9,"Víctor")+SUMIFS('Entrega'!$I$6:$I$9,'Entrega'!$B$6:$B$9,$A120,'Entrega'!$E$6:$E$9,"Ambos")+SUMIFS('Defensa'!$I$6:$I$10,'Defensa'!$B$6:$B$10,$A120,'Defensa'!$E$6:$E$10,"Víctor")+SUMIFS('Defensa'!$I$6:$I$10,'Defensa'!$B$6:$B$10,$A120,'Defensa'!$E$6:$E$10,"Ambos")</f>
+        <f>SUMIFS('S1'!$I$6:$I$32,'S1'!$B$6:$B$32,$A120,'S1'!$E$6:$E$32,"Víctor")+SUMIFS('S1'!$I$6:$I$32,'S1'!$B$6:$B$32,$A120,'S1'!$E$6:$E$32,"Ambos")+SUMIFS('S2'!$I$6:$I$23,'S2'!$B$6:$B$23,$A120,'S2'!$E$6:$E$23,"Víctor")+SUMIFS('S2'!$I$6:$I$23,'S2'!$B$6:$B$23,$A120,'S2'!$E$6:$E$23,"Ambos")+SUMIFS('S3'!$I$6:$I$24,'S3'!$B$6:$B$24,$A120,'S3'!$E$6:$E$24,"Víctor")+SUMIFS('S3'!$I$6:$I$24,'S3'!$B$6:$B$24,$A120,'S3'!$E$6:$E$24,"Ambos")+SUMIFS('S4'!$I$6:$I$22,'S4'!$B$6:$B$22,$A120,'S4'!$E$6:$E$22,"Víctor")+SUMIFS('S4'!$I$6:$I$22,'S4'!$B$6:$B$22,$A120,'S4'!$E$6:$E$22,"Ambos")+SUMIFS('S5'!$I$6:$I$20,'S5'!$B$6:$B$20,$A120,'S5'!$E$6:$E$20,"Víctor")+SUMIFS('S5'!$I$6:$I$20,'S5'!$B$6:$B$20,$A120,'S5'!$E$6:$E$20,"Ambos")+SUMIFS('S6'!$I$6:$I$17,'S6'!$B$6:$B$17,$A120,'S6'!$E$6:$E$17,"Víctor")+SUMIFS('S6'!$I$6:$I$17,'S6'!$B$6:$B$17,$A120,'S6'!$E$6:$E$17,"Ambos")+SUMIFS('S7'!$I$6:$I$19,'S7'!$B$6:$B$19,$A120,'S7'!$E$6:$E$19,"Víctor")+SUMIFS('S7'!$I$6:$I$19,'S7'!$B$6:$B$19,$A120,'S7'!$E$6:$E$19,"Ambos")+SUMIFS('S8'!$I$6:$I$23,'S8'!$B$6:$B$23,$A120,'S8'!$E$6:$E$23,"Víctor")+SUMIFS('S8'!$I$6:$I$23,'S8'!$B$6:$B$23,$A120,'S8'!$E$6:$E$23,"Ambos")+SUMIFS('S9'!$I$6:$I$15,'S9'!$B$6:$B$15,$A120,'S9'!$E$6:$E$15,"Víctor")+SUMIFS('S9'!$I$6:$I$15,'S9'!$B$6:$B$15,$A120,'S9'!$E$6:$E$15,"Ambos")+SUMIFS('S10'!$I$6:$I$13,'S10'!$B$6:$B$13,$A120,'S10'!$E$6:$E$13,"Víctor")+SUMIFS('S10'!$I$6:$I$13,'S10'!$B$6:$B$13,$A120,'S10'!$E$6:$E$13,"Ambos")+SUMIFS('Holgura'!$I$6:$I$11,'Holgura'!$B$6:$B$11,$A120,'Holgura'!$E$6:$E$11,"Víctor")+SUMIFS('Holgura'!$I$6:$I$11,'Holgura'!$B$6:$B$11,$A120,'Holgura'!$E$6:$E$11,"Ambos")+SUMIFS('Entrega'!$I$6:$I$9,'Entrega'!$B$6:$B$9,$A120,'Entrega'!$E$6:$E$9,"Víctor")+SUMIFS('Entrega'!$I$6:$I$9,'Entrega'!$B$6:$B$9,$A120,'Entrega'!$E$6:$E$9,"Ambos")+SUMIFS('Defensa'!$I$6:$I$10,'Defensa'!$B$6:$B$10,$A120,'Defensa'!$E$6:$E$10,"Víctor")+SUMIFS('Defensa'!$I$6:$I$10,'Defensa'!$B$6:$B$10,$A120,'Defensa'!$E$6:$E$10,"Ambos")</f>
         <v/>
       </c>
       <c r="E120" s="21">
-        <f>SUMIFS('S1'!$I$6:$I$32,'S1'!$B$6:$B$32,$A120,'S1'!$E$6:$E$32,"Diego")+SUMIFS('S1'!$I$6:$I$32,'S1'!$B$6:$B$32,$A120,'S1'!$E$6:$E$32,"Ambos")+SUMIFS('S2'!$I$6:$I$23,'S2'!$B$6:$B$23,$A120,'S2'!$E$6:$E$23,"Diego")+SUMIFS('S2'!$I$6:$I$23,'S2'!$B$6:$B$23,$A120,'S2'!$E$6:$E$23,"Ambos")+SUMIFS('S3'!$I$6:$I$19,'S3'!$B$6:$B$19,$A120,'S3'!$E$6:$E$19,"Diego")+SUMIFS('S3'!$I$6:$I$19,'S3'!$B$6:$B$19,$A120,'S3'!$E$6:$E$19,"Ambos")+SUMIFS('S4'!$I$6:$I$20,'S4'!$B$6:$B$20,$A120,'S4'!$E$6:$E$20,"Diego")+SUMIFS('S4'!$I$6:$I$20,'S4'!$B$6:$B$20,$A120,'S4'!$E$6:$E$20,"Ambos")+SUMIFS('S5'!$I$6:$I$20,'S5'!$B$6:$B$20,$A120,'S5'!$E$6:$E$20,"Diego")+SUMIFS('S5'!$I$6:$I$20,'S5'!$B$6:$B$20,$A120,'S5'!$E$6:$E$20,"Ambos")+SUMIFS('S6'!$I$6:$I$17,'S6'!$B$6:$B$17,$A120,'S6'!$E$6:$E$17,"Diego")+SUMIFS('S6'!$I$6:$I$17,'S6'!$B$6:$B$17,$A120,'S6'!$E$6:$E$17,"Ambos")+SUMIFS('S7'!$I$6:$I$19,'S7'!$B$6:$B$19,$A120,'S7'!$E$6:$E$19,"Diego")+SUMIFS('S7'!$I$6:$I$19,'S7'!$B$6:$B$19,$A120,'S7'!$E$6:$E$19,"Ambos")+SUMIFS('S8'!$I$6:$I$23,'S8'!$B$6:$B$23,$A120,'S8'!$E$6:$E$23,"Diego")+SUMIFS('S8'!$I$6:$I$23,'S8'!$B$6:$B$23,$A120,'S8'!$E$6:$E$23,"Ambos")+SUMIFS('S9'!$I$6:$I$15,'S9'!$B$6:$B$15,$A120,'S9'!$E$6:$E$15,"Diego")+SUMIFS('S9'!$I$6:$I$15,'S9'!$B$6:$B$15,$A120,'S9'!$E$6:$E$15,"Ambos")+SUMIFS('S10'!$I$6:$I$13,'S10'!$B$6:$B$13,$A120,'S10'!$E$6:$E$13,"Diego")+SUMIFS('S10'!$I$6:$I$13,'S10'!$B$6:$B$13,$A120,'S10'!$E$6:$E$13,"Ambos")+SUMIFS('Holgura'!$I$6:$I$11,'Holgura'!$B$6:$B$11,$A120,'Holgura'!$E$6:$E$11,"Diego")+SUMIFS('Holgura'!$I$6:$I$11,'Holgura'!$B$6:$B$11,$A120,'Holgura'!$E$6:$E$11,"Ambos")+SUMIFS('Entrega'!$I$6:$I$9,'Entrega'!$B$6:$B$9,$A120,'Entrega'!$E$6:$E$9,"Diego")+SUMIFS('Entrega'!$I$6:$I$9,'Entrega'!$B$6:$B$9,$A120,'Entrega'!$E$6:$E$9,"Ambos")+SUMIFS('Defensa'!$I$6:$I$10,'Defensa'!$B$6:$B$10,$A120,'Defensa'!$E$6:$E$10,"Diego")+SUMIFS('Defensa'!$I$6:$I$10,'Defensa'!$B$6:$B$10,$A120,'Defensa'!$E$6:$E$10,"Ambos")</f>
+        <f>SUMIFS('S1'!$I$6:$I$32,'S1'!$B$6:$B$32,$A120,'S1'!$E$6:$E$32,"Diego")+SUMIFS('S1'!$I$6:$I$32,'S1'!$B$6:$B$32,$A120,'S1'!$E$6:$E$32,"Ambos")+SUMIFS('S2'!$I$6:$I$23,'S2'!$B$6:$B$23,$A120,'S2'!$E$6:$E$23,"Diego")+SUMIFS('S2'!$I$6:$I$23,'S2'!$B$6:$B$23,$A120,'S2'!$E$6:$E$23,"Ambos")+SUMIFS('S3'!$I$6:$I$24,'S3'!$B$6:$B$24,$A120,'S3'!$E$6:$E$24,"Diego")+SUMIFS('S3'!$I$6:$I$24,'S3'!$B$6:$B$24,$A120,'S3'!$E$6:$E$24,"Ambos")+SUMIFS('S4'!$I$6:$I$22,'S4'!$B$6:$B$22,$A120,'S4'!$E$6:$E$22,"Diego")+SUMIFS('S4'!$I$6:$I$22,'S4'!$B$6:$B$22,$A120,'S4'!$E$6:$E$22,"Ambos")+SUMIFS('S5'!$I$6:$I$20,'S5'!$B$6:$B$20,$A120,'S5'!$E$6:$E$20,"Diego")+SUMIFS('S5'!$I$6:$I$20,'S5'!$B$6:$B$20,$A120,'S5'!$E$6:$E$20,"Ambos")+SUMIFS('S6'!$I$6:$I$17,'S6'!$B$6:$B$17,$A120,'S6'!$E$6:$E$17,"Diego")+SUMIFS('S6'!$I$6:$I$17,'S6'!$B$6:$B$17,$A120,'S6'!$E$6:$E$17,"Ambos")+SUMIFS('S7'!$I$6:$I$19,'S7'!$B$6:$B$19,$A120,'S7'!$E$6:$E$19,"Diego")+SUMIFS('S7'!$I$6:$I$19,'S7'!$B$6:$B$19,$A120,'S7'!$E$6:$E$19,"Ambos")+SUMIFS('S8'!$I$6:$I$23,'S8'!$B$6:$B$23,$A120,'S8'!$E$6:$E$23,"Diego")+SUMIFS('S8'!$I$6:$I$23,'S8'!$B$6:$B$23,$A120,'S8'!$E$6:$E$23,"Ambos")+SUMIFS('S9'!$I$6:$I$15,'S9'!$B$6:$B$15,$A120,'S9'!$E$6:$E$15,"Diego")+SUMIFS('S9'!$I$6:$I$15,'S9'!$B$6:$B$15,$A120,'S9'!$E$6:$E$15,"Ambos")+SUMIFS('S10'!$I$6:$I$13,'S10'!$B$6:$B$13,$A120,'S10'!$E$6:$E$13,"Diego")+SUMIFS('S10'!$I$6:$I$13,'S10'!$B$6:$B$13,$A120,'S10'!$E$6:$E$13,"Ambos")+SUMIFS('Holgura'!$I$6:$I$11,'Holgura'!$B$6:$B$11,$A120,'Holgura'!$E$6:$E$11,"Diego")+SUMIFS('Holgura'!$I$6:$I$11,'Holgura'!$B$6:$B$11,$A120,'Holgura'!$E$6:$E$11,"Ambos")+SUMIFS('Entrega'!$I$6:$I$9,'Entrega'!$B$6:$B$9,$A120,'Entrega'!$E$6:$E$9,"Diego")+SUMIFS('Entrega'!$I$6:$I$9,'Entrega'!$B$6:$B$9,$A120,'Entrega'!$E$6:$E$9,"Ambos")+SUMIFS('Defensa'!$I$6:$I$10,'Defensa'!$B$6:$B$10,$A120,'Defensa'!$E$6:$E$10,"Diego")+SUMIFS('Defensa'!$I$6:$I$10,'Defensa'!$B$6:$B$10,$A120,'Defensa'!$E$6:$E$10,"Ambos")</f>
         <v/>
       </c>
       <c r="F120" s="21">
-        <f>COUNTIFS('S1'!$B$6:$B$32,$A120,'S1'!$E$6:$E$32,"Víctor")+COUNTIFS('S1'!$B$6:$B$32,$A120,'S1'!$E$6:$E$32,"Ambos")+COUNTIFS('S2'!$B$6:$B$23,$A120,'S2'!$E$6:$E$23,"Víctor")+COUNTIFS('S2'!$B$6:$B$23,$A120,'S2'!$E$6:$E$23,"Ambos")+COUNTIFS('S3'!$B$6:$B$19,$A120,'S3'!$E$6:$E$19,"Víctor")+COUNTIFS('S3'!$B$6:$B$19,$A120,'S3'!$E$6:$E$19,"Ambos")+COUNTIFS('S4'!$B$6:$B$20,$A120,'S4'!$E$6:$E$20,"Víctor")+COUNTIFS('S4'!$B$6:$B$20,$A120,'S4'!$E$6:$E$20,"Ambos")+COUNTIFS('S5'!$B$6:$B$20,$A120,'S5'!$E$6:$E$20,"Víctor")+COUNTIFS('S5'!$B$6:$B$20,$A120,'S5'!$E$6:$E$20,"Ambos")+COUNTIFS('S6'!$B$6:$B$17,$A120,'S6'!$E$6:$E$17,"Víctor")+COUNTIFS('S6'!$B$6:$B$17,$A120,'S6'!$E$6:$E$17,"Ambos")+COUNTIFS('S7'!$B$6:$B$19,$A120,'S7'!$E$6:$E$19,"Víctor")+COUNTIFS('S7'!$B$6:$B$19,$A120,'S7'!$E$6:$E$19,"Ambos")+COUNTIFS('S8'!$B$6:$B$23,$A120,'S8'!$E$6:$E$23,"Víctor")+COUNTIFS('S8'!$B$6:$B$23,$A120,'S8'!$E$6:$E$23,"Ambos")+COUNTIFS('S9'!$B$6:$B$15,$A120,'S9'!$E$6:$E$15,"Víctor")+COUNTIFS('S9'!$B$6:$B$15,$A120,'S9'!$E$6:$E$15,"Ambos")+COUNTIFS('S10'!$B$6:$B$13,$A120,'S10'!$E$6:$E$13,"Víctor")+COUNTIFS('S10'!$B$6:$B$13,$A120,'S10'!$E$6:$E$13,"Ambos")+COUNTIFS('Holgura'!$B$6:$B$11,$A120,'Holgura'!$E$6:$E$11,"Víctor")+COUNTIFS('Holgura'!$B$6:$B$11,$A120,'Holgura'!$E$6:$E$11,"Ambos")+COUNTIFS('Entrega'!$B$6:$B$9,$A120,'Entrega'!$E$6:$E$9,"Víctor")+COUNTIFS('Entrega'!$B$6:$B$9,$A120,'Entrega'!$E$6:$E$9,"Ambos")+COUNTIFS('Defensa'!$B$6:$B$10,$A120,'Defensa'!$E$6:$E$10,"Víctor")+COUNTIFS('Defensa'!$B$6:$B$10,$A120,'Defensa'!$E$6:$E$10,"Ambos")</f>
+        <f>COUNTIFS('S1'!$B$6:$B$32,$A120,'S1'!$E$6:$E$32,"Víctor")+COUNTIFS('S1'!$B$6:$B$32,$A120,'S1'!$E$6:$E$32,"Ambos")+COUNTIFS('S2'!$B$6:$B$23,$A120,'S2'!$E$6:$E$23,"Víctor")+COUNTIFS('S2'!$B$6:$B$23,$A120,'S2'!$E$6:$E$23,"Ambos")+COUNTIFS('S3'!$B$6:$B$24,$A120,'S3'!$E$6:$E$24,"Víctor")+COUNTIFS('S3'!$B$6:$B$24,$A120,'S3'!$E$6:$E$24,"Ambos")+COUNTIFS('S4'!$B$6:$B$22,$A120,'S4'!$E$6:$E$22,"Víctor")+COUNTIFS('S4'!$B$6:$B$22,$A120,'S4'!$E$6:$E$22,"Ambos")+COUNTIFS('S5'!$B$6:$B$20,$A120,'S5'!$E$6:$E$20,"Víctor")+COUNTIFS('S5'!$B$6:$B$20,$A120,'S5'!$E$6:$E$20,"Ambos")+COUNTIFS('S6'!$B$6:$B$17,$A120,'S6'!$E$6:$E$17,"Víctor")+COUNTIFS('S6'!$B$6:$B$17,$A120,'S6'!$E$6:$E$17,"Ambos")+COUNTIFS('S7'!$B$6:$B$19,$A120,'S7'!$E$6:$E$19,"Víctor")+COUNTIFS('S7'!$B$6:$B$19,$A120,'S7'!$E$6:$E$19,"Ambos")+COUNTIFS('S8'!$B$6:$B$23,$A120,'S8'!$E$6:$E$23,"Víctor")+COUNTIFS('S8'!$B$6:$B$23,$A120,'S8'!$E$6:$E$23,"Ambos")+COUNTIFS('S9'!$B$6:$B$15,$A120,'S9'!$E$6:$E$15,"Víctor")+COUNTIFS('S9'!$B$6:$B$15,$A120,'S9'!$E$6:$E$15,"Ambos")+COUNTIFS('S10'!$B$6:$B$13,$A120,'S10'!$E$6:$E$13,"Víctor")+COUNTIFS('S10'!$B$6:$B$13,$A120,'S10'!$E$6:$E$13,"Ambos")+COUNTIFS('Holgura'!$B$6:$B$11,$A120,'Holgura'!$E$6:$E$11,"Víctor")+COUNTIFS('Holgura'!$B$6:$B$11,$A120,'Holgura'!$E$6:$E$11,"Ambos")+COUNTIFS('Entrega'!$B$6:$B$9,$A120,'Entrega'!$E$6:$E$9,"Víctor")+COUNTIFS('Entrega'!$B$6:$B$9,$A120,'Entrega'!$E$6:$E$9,"Ambos")+COUNTIFS('Defensa'!$B$6:$B$10,$A120,'Defensa'!$E$6:$E$10,"Víctor")+COUNTIFS('Defensa'!$B$6:$B$10,$A120,'Defensa'!$E$6:$E$10,"Ambos")</f>
         <v/>
       </c>
       <c r="G120" s="21">
-        <f>COUNTIFS('S1'!$B$6:$B$32,$A120,'S1'!$E$6:$E$32,"Diego")+COUNTIFS('S1'!$B$6:$B$32,$A120,'S1'!$E$6:$E$32,"Ambos")+COUNTIFS('S2'!$B$6:$B$23,$A120,'S2'!$E$6:$E$23,"Diego")+COUNTIFS('S2'!$B$6:$B$23,$A120,'S2'!$E$6:$E$23,"Ambos")+COUNTIFS('S3'!$B$6:$B$19,$A120,'S3'!$E$6:$E$19,"Diego")+COUNTIFS('S3'!$B$6:$B$19,$A120,'S3'!$E$6:$E$19,"Ambos")+COUNTIFS('S4'!$B$6:$B$20,$A120,'S4'!$E$6:$E$20,"Diego")+COUNTIFS('S4'!$B$6:$B$20,$A120,'S4'!$E$6:$E$20,"Ambos")+COUNTIFS('S5'!$B$6:$B$20,$A120,'S5'!$E$6:$E$20,"Diego")+COUNTIFS('S5'!$B$6:$B$20,$A120,'S5'!$E$6:$E$20,"Ambos")+COUNTIFS('S6'!$B$6:$B$17,$A120,'S6'!$E$6:$E$17,"Diego")+COUNTIFS('S6'!$B$6:$B$17,$A120,'S6'!$E$6:$E$17,"Ambos")+COUNTIFS('S7'!$B$6:$B$19,$A120,'S7'!$E$6:$E$19,"Diego")+COUNTIFS('S7'!$B$6:$B$19,$A120,'S7'!$E$6:$E$19,"Ambos")+COUNTIFS('S8'!$B$6:$B$23,$A120,'S8'!$E$6:$E$23,"Diego")+COUNTIFS('S8'!$B$6:$B$23,$A120,'S8'!$E$6:$E$23,"Ambos")+COUNTIFS('S9'!$B$6:$B$15,$A120,'S9'!$E$6:$E$15,"Diego")+COUNTIFS('S9'!$B$6:$B$15,$A120,'S9'!$E$6:$E$15,"Ambos")+COUNTIFS('S10'!$B$6:$B$13,$A120,'S10'!$E$6:$E$13,"Diego")+COUNTIFS('S10'!$B$6:$B$13,$A120,'S10'!$E$6:$E$13,"Ambos")+COUNTIFS('Holgura'!$B$6:$B$11,$A120,'Holgura'!$E$6:$E$11,"Diego")+COUNTIFS('Holgura'!$B$6:$B$11,$A120,'Holgura'!$E$6:$E$11,"Ambos")+COUNTIFS('Entrega'!$B$6:$B$9,$A120,'Entrega'!$E$6:$E$9,"Diego")+COUNTIFS('Entrega'!$B$6:$B$9,$A120,'Entrega'!$E$6:$E$9,"Ambos")+COUNTIFS('Defensa'!$B$6:$B$10,$A120,'Defensa'!$E$6:$E$10,"Diego")+COUNTIFS('Defensa'!$B$6:$B$10,$A120,'Defensa'!$E$6:$E$10,"Ambos")</f>
+        <f>COUNTIFS('S1'!$B$6:$B$32,$A120,'S1'!$E$6:$E$32,"Diego")+COUNTIFS('S1'!$B$6:$B$32,$A120,'S1'!$E$6:$E$32,"Ambos")+COUNTIFS('S2'!$B$6:$B$23,$A120,'S2'!$E$6:$E$23,"Diego")+COUNTIFS('S2'!$B$6:$B$23,$A120,'S2'!$E$6:$E$23,"Ambos")+COUNTIFS('S3'!$B$6:$B$24,$A120,'S3'!$E$6:$E$24,"Diego")+COUNTIFS('S3'!$B$6:$B$24,$A120,'S3'!$E$6:$E$24,"Ambos")+COUNTIFS('S4'!$B$6:$B$22,$A120,'S4'!$E$6:$E$22,"Diego")+COUNTIFS('S4'!$B$6:$B$22,$A120,'S4'!$E$6:$E$22,"Ambos")+COUNTIFS('S5'!$B$6:$B$20,$A120,'S5'!$E$6:$E$20,"Diego")+COUNTIFS('S5'!$B$6:$B$20,$A120,'S5'!$E$6:$E$20,"Ambos")+COUNTIFS('S6'!$B$6:$B$17,$A120,'S6'!$E$6:$E$17,"Diego")+COUNTIFS('S6'!$B$6:$B$17,$A120,'S6'!$E$6:$E$17,"Ambos")+COUNTIFS('S7'!$B$6:$B$19,$A120,'S7'!$E$6:$E$19,"Diego")+COUNTIFS('S7'!$B$6:$B$19,$A120,'S7'!$E$6:$E$19,"Ambos")+COUNTIFS('S8'!$B$6:$B$23,$A120,'S8'!$E$6:$E$23,"Diego")+COUNTIFS('S8'!$B$6:$B$23,$A120,'S8'!$E$6:$E$23,"Ambos")+COUNTIFS('S9'!$B$6:$B$15,$A120,'S9'!$E$6:$E$15,"Diego")+COUNTIFS('S9'!$B$6:$B$15,$A120,'S9'!$E$6:$E$15,"Ambos")+COUNTIFS('S10'!$B$6:$B$13,$A120,'S10'!$E$6:$E$13,"Diego")+COUNTIFS('S10'!$B$6:$B$13,$A120,'S10'!$E$6:$E$13,"Ambos")+COUNTIFS('Holgura'!$B$6:$B$11,$A120,'Holgura'!$E$6:$E$11,"Diego")+COUNTIFS('Holgura'!$B$6:$B$11,$A120,'Holgura'!$E$6:$E$11,"Ambos")+COUNTIFS('Entrega'!$B$6:$B$9,$A120,'Entrega'!$E$6:$E$9,"Diego")+COUNTIFS('Entrega'!$B$6:$B$9,$A120,'Entrega'!$E$6:$E$9,"Ambos")+COUNTIFS('Defensa'!$B$6:$B$10,$A120,'Defensa'!$E$6:$E$10,"Diego")+COUNTIFS('Defensa'!$B$6:$B$10,$A120,'Defensa'!$E$6:$E$10,"Ambos")</f>
         <v/>
       </c>
     </row>
@@ -12044,19 +12065,19 @@
         <v/>
       </c>
       <c r="D121" s="21">
-        <f>SUMIFS('S1'!$I$6:$I$32,'S1'!$B$6:$B$32,$A121,'S1'!$E$6:$E$32,"Víctor")+SUMIFS('S1'!$I$6:$I$32,'S1'!$B$6:$B$32,$A121,'S1'!$E$6:$E$32,"Ambos")+SUMIFS('S2'!$I$6:$I$23,'S2'!$B$6:$B$23,$A121,'S2'!$E$6:$E$23,"Víctor")+SUMIFS('S2'!$I$6:$I$23,'S2'!$B$6:$B$23,$A121,'S2'!$E$6:$E$23,"Ambos")+SUMIFS('S3'!$I$6:$I$19,'S3'!$B$6:$B$19,$A121,'S3'!$E$6:$E$19,"Víctor")+SUMIFS('S3'!$I$6:$I$19,'S3'!$B$6:$B$19,$A121,'S3'!$E$6:$E$19,"Ambos")+SUMIFS('S4'!$I$6:$I$20,'S4'!$B$6:$B$20,$A121,'S4'!$E$6:$E$20,"Víctor")+SUMIFS('S4'!$I$6:$I$20,'S4'!$B$6:$B$20,$A121,'S4'!$E$6:$E$20,"Ambos")+SUMIFS('S5'!$I$6:$I$20,'S5'!$B$6:$B$20,$A121,'S5'!$E$6:$E$20,"Víctor")+SUMIFS('S5'!$I$6:$I$20,'S5'!$B$6:$B$20,$A121,'S5'!$E$6:$E$20,"Ambos")+SUMIFS('S6'!$I$6:$I$17,'S6'!$B$6:$B$17,$A121,'S6'!$E$6:$E$17,"Víctor")+SUMIFS('S6'!$I$6:$I$17,'S6'!$B$6:$B$17,$A121,'S6'!$E$6:$E$17,"Ambos")+SUMIFS('S7'!$I$6:$I$19,'S7'!$B$6:$B$19,$A121,'S7'!$E$6:$E$19,"Víctor")+SUMIFS('S7'!$I$6:$I$19,'S7'!$B$6:$B$19,$A121,'S7'!$E$6:$E$19,"Ambos")+SUMIFS('S8'!$I$6:$I$23,'S8'!$B$6:$B$23,$A121,'S8'!$E$6:$E$23,"Víctor")+SUMIFS('S8'!$I$6:$I$23,'S8'!$B$6:$B$23,$A121,'S8'!$E$6:$E$23,"Ambos")+SUMIFS('S9'!$I$6:$I$15,'S9'!$B$6:$B$15,$A121,'S9'!$E$6:$E$15,"Víctor")+SUMIFS('S9'!$I$6:$I$15,'S9'!$B$6:$B$15,$A121,'S9'!$E$6:$E$15,"Ambos")+SUMIFS('S10'!$I$6:$I$13,'S10'!$B$6:$B$13,$A121,'S10'!$E$6:$E$13,"Víctor")+SUMIFS('S10'!$I$6:$I$13,'S10'!$B$6:$B$13,$A121,'S10'!$E$6:$E$13,"Ambos")+SUMIFS('Holgura'!$I$6:$I$11,'Holgura'!$B$6:$B$11,$A121,'Holgura'!$E$6:$E$11,"Víctor")+SUMIFS('Holgura'!$I$6:$I$11,'Holgura'!$B$6:$B$11,$A121,'Holgura'!$E$6:$E$11,"Ambos")+SUMIFS('Entrega'!$I$6:$I$9,'Entrega'!$B$6:$B$9,$A121,'Entrega'!$E$6:$E$9,"Víctor")+SUMIFS('Entrega'!$I$6:$I$9,'Entrega'!$B$6:$B$9,$A121,'Entrega'!$E$6:$E$9,"Ambos")+SUMIFS('Defensa'!$I$6:$I$10,'Defensa'!$B$6:$B$10,$A121,'Defensa'!$E$6:$E$10,"Víctor")+SUMIFS('Defensa'!$I$6:$I$10,'Defensa'!$B$6:$B$10,$A121,'Defensa'!$E$6:$E$10,"Ambos")</f>
+        <f>SUMIFS('S1'!$I$6:$I$32,'S1'!$B$6:$B$32,$A121,'S1'!$E$6:$E$32,"Víctor")+SUMIFS('S1'!$I$6:$I$32,'S1'!$B$6:$B$32,$A121,'S1'!$E$6:$E$32,"Ambos")+SUMIFS('S2'!$I$6:$I$23,'S2'!$B$6:$B$23,$A121,'S2'!$E$6:$E$23,"Víctor")+SUMIFS('S2'!$I$6:$I$23,'S2'!$B$6:$B$23,$A121,'S2'!$E$6:$E$23,"Ambos")+SUMIFS('S3'!$I$6:$I$24,'S3'!$B$6:$B$24,$A121,'S3'!$E$6:$E$24,"Víctor")+SUMIFS('S3'!$I$6:$I$24,'S3'!$B$6:$B$24,$A121,'S3'!$E$6:$E$24,"Ambos")+SUMIFS('S4'!$I$6:$I$22,'S4'!$B$6:$B$22,$A121,'S4'!$E$6:$E$22,"Víctor")+SUMIFS('S4'!$I$6:$I$22,'S4'!$B$6:$B$22,$A121,'S4'!$E$6:$E$22,"Ambos")+SUMIFS('S5'!$I$6:$I$20,'S5'!$B$6:$B$20,$A121,'S5'!$E$6:$E$20,"Víctor")+SUMIFS('S5'!$I$6:$I$20,'S5'!$B$6:$B$20,$A121,'S5'!$E$6:$E$20,"Ambos")+SUMIFS('S6'!$I$6:$I$17,'S6'!$B$6:$B$17,$A121,'S6'!$E$6:$E$17,"Víctor")+SUMIFS('S6'!$I$6:$I$17,'S6'!$B$6:$B$17,$A121,'S6'!$E$6:$E$17,"Ambos")+SUMIFS('S7'!$I$6:$I$19,'S7'!$B$6:$B$19,$A121,'S7'!$E$6:$E$19,"Víctor")+SUMIFS('S7'!$I$6:$I$19,'S7'!$B$6:$B$19,$A121,'S7'!$E$6:$E$19,"Ambos")+SUMIFS('S8'!$I$6:$I$23,'S8'!$B$6:$B$23,$A121,'S8'!$E$6:$E$23,"Víctor")+SUMIFS('S8'!$I$6:$I$23,'S8'!$B$6:$B$23,$A121,'S8'!$E$6:$E$23,"Ambos")+SUMIFS('S9'!$I$6:$I$15,'S9'!$B$6:$B$15,$A121,'S9'!$E$6:$E$15,"Víctor")+SUMIFS('S9'!$I$6:$I$15,'S9'!$B$6:$B$15,$A121,'S9'!$E$6:$E$15,"Ambos")+SUMIFS('S10'!$I$6:$I$13,'S10'!$B$6:$B$13,$A121,'S10'!$E$6:$E$13,"Víctor")+SUMIFS('S10'!$I$6:$I$13,'S10'!$B$6:$B$13,$A121,'S10'!$E$6:$E$13,"Ambos")+SUMIFS('Holgura'!$I$6:$I$11,'Holgura'!$B$6:$B$11,$A121,'Holgura'!$E$6:$E$11,"Víctor")+SUMIFS('Holgura'!$I$6:$I$11,'Holgura'!$B$6:$B$11,$A121,'Holgura'!$E$6:$E$11,"Ambos")+SUMIFS('Entrega'!$I$6:$I$9,'Entrega'!$B$6:$B$9,$A121,'Entrega'!$E$6:$E$9,"Víctor")+SUMIFS('Entrega'!$I$6:$I$9,'Entrega'!$B$6:$B$9,$A121,'Entrega'!$E$6:$E$9,"Ambos")+SUMIFS('Defensa'!$I$6:$I$10,'Defensa'!$B$6:$B$10,$A121,'Defensa'!$E$6:$E$10,"Víctor")+SUMIFS('Defensa'!$I$6:$I$10,'Defensa'!$B$6:$B$10,$A121,'Defensa'!$E$6:$E$10,"Ambos")</f>
         <v/>
       </c>
       <c r="E121" s="21">
-        <f>SUMIFS('S1'!$I$6:$I$32,'S1'!$B$6:$B$32,$A121,'S1'!$E$6:$E$32,"Diego")+SUMIFS('S1'!$I$6:$I$32,'S1'!$B$6:$B$32,$A121,'S1'!$E$6:$E$32,"Ambos")+SUMIFS('S2'!$I$6:$I$23,'S2'!$B$6:$B$23,$A121,'S2'!$E$6:$E$23,"Diego")+SUMIFS('S2'!$I$6:$I$23,'S2'!$B$6:$B$23,$A121,'S2'!$E$6:$E$23,"Ambos")+SUMIFS('S3'!$I$6:$I$19,'S3'!$B$6:$B$19,$A121,'S3'!$E$6:$E$19,"Diego")+SUMIFS('S3'!$I$6:$I$19,'S3'!$B$6:$B$19,$A121,'S3'!$E$6:$E$19,"Ambos")+SUMIFS('S4'!$I$6:$I$20,'S4'!$B$6:$B$20,$A121,'S4'!$E$6:$E$20,"Diego")+SUMIFS('S4'!$I$6:$I$20,'S4'!$B$6:$B$20,$A121,'S4'!$E$6:$E$20,"Ambos")+SUMIFS('S5'!$I$6:$I$20,'S5'!$B$6:$B$20,$A121,'S5'!$E$6:$E$20,"Diego")+SUMIFS('S5'!$I$6:$I$20,'S5'!$B$6:$B$20,$A121,'S5'!$E$6:$E$20,"Ambos")+SUMIFS('S6'!$I$6:$I$17,'S6'!$B$6:$B$17,$A121,'S6'!$E$6:$E$17,"Diego")+SUMIFS('S6'!$I$6:$I$17,'S6'!$B$6:$B$17,$A121,'S6'!$E$6:$E$17,"Ambos")+SUMIFS('S7'!$I$6:$I$19,'S7'!$B$6:$B$19,$A121,'S7'!$E$6:$E$19,"Diego")+SUMIFS('S7'!$I$6:$I$19,'S7'!$B$6:$B$19,$A121,'S7'!$E$6:$E$19,"Ambos")+SUMIFS('S8'!$I$6:$I$23,'S8'!$B$6:$B$23,$A121,'S8'!$E$6:$E$23,"Diego")+SUMIFS('S8'!$I$6:$I$23,'S8'!$B$6:$B$23,$A121,'S8'!$E$6:$E$23,"Ambos")+SUMIFS('S9'!$I$6:$I$15,'S9'!$B$6:$B$15,$A121,'S9'!$E$6:$E$15,"Diego")+SUMIFS('S9'!$I$6:$I$15,'S9'!$B$6:$B$15,$A121,'S9'!$E$6:$E$15,"Ambos")+SUMIFS('S10'!$I$6:$I$13,'S10'!$B$6:$B$13,$A121,'S10'!$E$6:$E$13,"Diego")+SUMIFS('S10'!$I$6:$I$13,'S10'!$B$6:$B$13,$A121,'S10'!$E$6:$E$13,"Ambos")+SUMIFS('Holgura'!$I$6:$I$11,'Holgura'!$B$6:$B$11,$A121,'Holgura'!$E$6:$E$11,"Diego")+SUMIFS('Holgura'!$I$6:$I$11,'Holgura'!$B$6:$B$11,$A121,'Holgura'!$E$6:$E$11,"Ambos")+SUMIFS('Entrega'!$I$6:$I$9,'Entrega'!$B$6:$B$9,$A121,'Entrega'!$E$6:$E$9,"Diego")+SUMIFS('Entrega'!$I$6:$I$9,'Entrega'!$B$6:$B$9,$A121,'Entrega'!$E$6:$E$9,"Ambos")+SUMIFS('Defensa'!$I$6:$I$10,'Defensa'!$B$6:$B$10,$A121,'Defensa'!$E$6:$E$10,"Diego")+SUMIFS('Defensa'!$I$6:$I$10,'Defensa'!$B$6:$B$10,$A121,'Defensa'!$E$6:$E$10,"Ambos")</f>
+        <f>SUMIFS('S1'!$I$6:$I$32,'S1'!$B$6:$B$32,$A121,'S1'!$E$6:$E$32,"Diego")+SUMIFS('S1'!$I$6:$I$32,'S1'!$B$6:$B$32,$A121,'S1'!$E$6:$E$32,"Ambos")+SUMIFS('S2'!$I$6:$I$23,'S2'!$B$6:$B$23,$A121,'S2'!$E$6:$E$23,"Diego")+SUMIFS('S2'!$I$6:$I$23,'S2'!$B$6:$B$23,$A121,'S2'!$E$6:$E$23,"Ambos")+SUMIFS('S3'!$I$6:$I$24,'S3'!$B$6:$B$24,$A121,'S3'!$E$6:$E$24,"Diego")+SUMIFS('S3'!$I$6:$I$24,'S3'!$B$6:$B$24,$A121,'S3'!$E$6:$E$24,"Ambos")+SUMIFS('S4'!$I$6:$I$22,'S4'!$B$6:$B$22,$A121,'S4'!$E$6:$E$22,"Diego")+SUMIFS('S4'!$I$6:$I$22,'S4'!$B$6:$B$22,$A121,'S4'!$E$6:$E$22,"Ambos")+SUMIFS('S5'!$I$6:$I$20,'S5'!$B$6:$B$20,$A121,'S5'!$E$6:$E$20,"Diego")+SUMIFS('S5'!$I$6:$I$20,'S5'!$B$6:$B$20,$A121,'S5'!$E$6:$E$20,"Ambos")+SUMIFS('S6'!$I$6:$I$17,'S6'!$B$6:$B$17,$A121,'S6'!$E$6:$E$17,"Diego")+SUMIFS('S6'!$I$6:$I$17,'S6'!$B$6:$B$17,$A121,'S6'!$E$6:$E$17,"Ambos")+SUMIFS('S7'!$I$6:$I$19,'S7'!$B$6:$B$19,$A121,'S7'!$E$6:$E$19,"Diego")+SUMIFS('S7'!$I$6:$I$19,'S7'!$B$6:$B$19,$A121,'S7'!$E$6:$E$19,"Ambos")+SUMIFS('S8'!$I$6:$I$23,'S8'!$B$6:$B$23,$A121,'S8'!$E$6:$E$23,"Diego")+SUMIFS('S8'!$I$6:$I$23,'S8'!$B$6:$B$23,$A121,'S8'!$E$6:$E$23,"Ambos")+SUMIFS('S9'!$I$6:$I$15,'S9'!$B$6:$B$15,$A121,'S9'!$E$6:$E$15,"Diego")+SUMIFS('S9'!$I$6:$I$15,'S9'!$B$6:$B$15,$A121,'S9'!$E$6:$E$15,"Ambos")+SUMIFS('S10'!$I$6:$I$13,'S10'!$B$6:$B$13,$A121,'S10'!$E$6:$E$13,"Diego")+SUMIFS('S10'!$I$6:$I$13,'S10'!$B$6:$B$13,$A121,'S10'!$E$6:$E$13,"Ambos")+SUMIFS('Holgura'!$I$6:$I$11,'Holgura'!$B$6:$B$11,$A121,'Holgura'!$E$6:$E$11,"Diego")+SUMIFS('Holgura'!$I$6:$I$11,'Holgura'!$B$6:$B$11,$A121,'Holgura'!$E$6:$E$11,"Ambos")+SUMIFS('Entrega'!$I$6:$I$9,'Entrega'!$B$6:$B$9,$A121,'Entrega'!$E$6:$E$9,"Diego")+SUMIFS('Entrega'!$I$6:$I$9,'Entrega'!$B$6:$B$9,$A121,'Entrega'!$E$6:$E$9,"Ambos")+SUMIFS('Defensa'!$I$6:$I$10,'Defensa'!$B$6:$B$10,$A121,'Defensa'!$E$6:$E$10,"Diego")+SUMIFS('Defensa'!$I$6:$I$10,'Defensa'!$B$6:$B$10,$A121,'Defensa'!$E$6:$E$10,"Ambos")</f>
         <v/>
       </c>
       <c r="F121" s="21">
-        <f>COUNTIFS('S1'!$B$6:$B$32,$A121,'S1'!$E$6:$E$32,"Víctor")+COUNTIFS('S1'!$B$6:$B$32,$A121,'S1'!$E$6:$E$32,"Ambos")+COUNTIFS('S2'!$B$6:$B$23,$A121,'S2'!$E$6:$E$23,"Víctor")+COUNTIFS('S2'!$B$6:$B$23,$A121,'S2'!$E$6:$E$23,"Ambos")+COUNTIFS('S3'!$B$6:$B$19,$A121,'S3'!$E$6:$E$19,"Víctor")+COUNTIFS('S3'!$B$6:$B$19,$A121,'S3'!$E$6:$E$19,"Ambos")+COUNTIFS('S4'!$B$6:$B$20,$A121,'S4'!$E$6:$E$20,"Víctor")+COUNTIFS('S4'!$B$6:$B$20,$A121,'S4'!$E$6:$E$20,"Ambos")+COUNTIFS('S5'!$B$6:$B$20,$A121,'S5'!$E$6:$E$20,"Víctor")+COUNTIFS('S5'!$B$6:$B$20,$A121,'S5'!$E$6:$E$20,"Ambos")+COUNTIFS('S6'!$B$6:$B$17,$A121,'S6'!$E$6:$E$17,"Víctor")+COUNTIFS('S6'!$B$6:$B$17,$A121,'S6'!$E$6:$E$17,"Ambos")+COUNTIFS('S7'!$B$6:$B$19,$A121,'S7'!$E$6:$E$19,"Víctor")+COUNTIFS('S7'!$B$6:$B$19,$A121,'S7'!$E$6:$E$19,"Ambos")+COUNTIFS('S8'!$B$6:$B$23,$A121,'S8'!$E$6:$E$23,"Víctor")+COUNTIFS('S8'!$B$6:$B$23,$A121,'S8'!$E$6:$E$23,"Ambos")+COUNTIFS('S9'!$B$6:$B$15,$A121,'S9'!$E$6:$E$15,"Víctor")+COUNTIFS('S9'!$B$6:$B$15,$A121,'S9'!$E$6:$E$15,"Ambos")+COUNTIFS('S10'!$B$6:$B$13,$A121,'S10'!$E$6:$E$13,"Víctor")+COUNTIFS('S10'!$B$6:$B$13,$A121,'S10'!$E$6:$E$13,"Ambos")+COUNTIFS('Holgura'!$B$6:$B$11,$A121,'Holgura'!$E$6:$E$11,"Víctor")+COUNTIFS('Holgura'!$B$6:$B$11,$A121,'Holgura'!$E$6:$E$11,"Ambos")+COUNTIFS('Entrega'!$B$6:$B$9,$A121,'Entrega'!$E$6:$E$9,"Víctor")+COUNTIFS('Entrega'!$B$6:$B$9,$A121,'Entrega'!$E$6:$E$9,"Ambos")+COUNTIFS('Defensa'!$B$6:$B$10,$A121,'Defensa'!$E$6:$E$10,"Víctor")+COUNTIFS('Defensa'!$B$6:$B$10,$A121,'Defensa'!$E$6:$E$10,"Ambos")</f>
+        <f>COUNTIFS('S1'!$B$6:$B$32,$A121,'S1'!$E$6:$E$32,"Víctor")+COUNTIFS('S1'!$B$6:$B$32,$A121,'S1'!$E$6:$E$32,"Ambos")+COUNTIFS('S2'!$B$6:$B$23,$A121,'S2'!$E$6:$E$23,"Víctor")+COUNTIFS('S2'!$B$6:$B$23,$A121,'S2'!$E$6:$E$23,"Ambos")+COUNTIFS('S3'!$B$6:$B$24,$A121,'S3'!$E$6:$E$24,"Víctor")+COUNTIFS('S3'!$B$6:$B$24,$A121,'S3'!$E$6:$E$24,"Ambos")+COUNTIFS('S4'!$B$6:$B$22,$A121,'S4'!$E$6:$E$22,"Víctor")+COUNTIFS('S4'!$B$6:$B$22,$A121,'S4'!$E$6:$E$22,"Ambos")+COUNTIFS('S5'!$B$6:$B$20,$A121,'S5'!$E$6:$E$20,"Víctor")+COUNTIFS('S5'!$B$6:$B$20,$A121,'S5'!$E$6:$E$20,"Ambos")+COUNTIFS('S6'!$B$6:$B$17,$A121,'S6'!$E$6:$E$17,"Víctor")+COUNTIFS('S6'!$B$6:$B$17,$A121,'S6'!$E$6:$E$17,"Ambos")+COUNTIFS('S7'!$B$6:$B$19,$A121,'S7'!$E$6:$E$19,"Víctor")+COUNTIFS('S7'!$B$6:$B$19,$A121,'S7'!$E$6:$E$19,"Ambos")+COUNTIFS('S8'!$B$6:$B$23,$A121,'S8'!$E$6:$E$23,"Víctor")+COUNTIFS('S8'!$B$6:$B$23,$A121,'S8'!$E$6:$E$23,"Ambos")+COUNTIFS('S9'!$B$6:$B$15,$A121,'S9'!$E$6:$E$15,"Víctor")+COUNTIFS('S9'!$B$6:$B$15,$A121,'S9'!$E$6:$E$15,"Ambos")+COUNTIFS('S10'!$B$6:$B$13,$A121,'S10'!$E$6:$E$13,"Víctor")+COUNTIFS('S10'!$B$6:$B$13,$A121,'S10'!$E$6:$E$13,"Ambos")+COUNTIFS('Holgura'!$B$6:$B$11,$A121,'Holgura'!$E$6:$E$11,"Víctor")+COUNTIFS('Holgura'!$B$6:$B$11,$A121,'Holgura'!$E$6:$E$11,"Ambos")+COUNTIFS('Entrega'!$B$6:$B$9,$A121,'Entrega'!$E$6:$E$9,"Víctor")+COUNTIFS('Entrega'!$B$6:$B$9,$A121,'Entrega'!$E$6:$E$9,"Ambos")+COUNTIFS('Defensa'!$B$6:$B$10,$A121,'Defensa'!$E$6:$E$10,"Víctor")+COUNTIFS('Defensa'!$B$6:$B$10,$A121,'Defensa'!$E$6:$E$10,"Ambos")</f>
         <v/>
       </c>
       <c r="G121" s="21">
-        <f>COUNTIFS('S1'!$B$6:$B$32,$A121,'S1'!$E$6:$E$32,"Diego")+COUNTIFS('S1'!$B$6:$B$32,$A121,'S1'!$E$6:$E$32,"Ambos")+COUNTIFS('S2'!$B$6:$B$23,$A121,'S2'!$E$6:$E$23,"Diego")+COUNTIFS('S2'!$B$6:$B$23,$A121,'S2'!$E$6:$E$23,"Ambos")+COUNTIFS('S3'!$B$6:$B$19,$A121,'S3'!$E$6:$E$19,"Diego")+COUNTIFS('S3'!$B$6:$B$19,$A121,'S3'!$E$6:$E$19,"Ambos")+COUNTIFS('S4'!$B$6:$B$20,$A121,'S4'!$E$6:$E$20,"Diego")+COUNTIFS('S4'!$B$6:$B$20,$A121,'S4'!$E$6:$E$20,"Ambos")+COUNTIFS('S5'!$B$6:$B$20,$A121,'S5'!$E$6:$E$20,"Diego")+COUNTIFS('S5'!$B$6:$B$20,$A121,'S5'!$E$6:$E$20,"Ambos")+COUNTIFS('S6'!$B$6:$B$17,$A121,'S6'!$E$6:$E$17,"Diego")+COUNTIFS('S6'!$B$6:$B$17,$A121,'S6'!$E$6:$E$17,"Ambos")+COUNTIFS('S7'!$B$6:$B$19,$A121,'S7'!$E$6:$E$19,"Diego")+COUNTIFS('S7'!$B$6:$B$19,$A121,'S7'!$E$6:$E$19,"Ambos")+COUNTIFS('S8'!$B$6:$B$23,$A121,'S8'!$E$6:$E$23,"Diego")+COUNTIFS('S8'!$B$6:$B$23,$A121,'S8'!$E$6:$E$23,"Ambos")+COUNTIFS('S9'!$B$6:$B$15,$A121,'S9'!$E$6:$E$15,"Diego")+COUNTIFS('S9'!$B$6:$B$15,$A121,'S9'!$E$6:$E$15,"Ambos")+COUNTIFS('S10'!$B$6:$B$13,$A121,'S10'!$E$6:$E$13,"Diego")+COUNTIFS('S10'!$B$6:$B$13,$A121,'S10'!$E$6:$E$13,"Ambos")+COUNTIFS('Holgura'!$B$6:$B$11,$A121,'Holgura'!$E$6:$E$11,"Diego")+COUNTIFS('Holgura'!$B$6:$B$11,$A121,'Holgura'!$E$6:$E$11,"Ambos")+COUNTIFS('Entrega'!$B$6:$B$9,$A121,'Entrega'!$E$6:$E$9,"Diego")+COUNTIFS('Entrega'!$B$6:$B$9,$A121,'Entrega'!$E$6:$E$9,"Ambos")+COUNTIFS('Defensa'!$B$6:$B$10,$A121,'Defensa'!$E$6:$E$10,"Diego")+COUNTIFS('Defensa'!$B$6:$B$10,$A121,'Defensa'!$E$6:$E$10,"Ambos")</f>
+        <f>COUNTIFS('S1'!$B$6:$B$32,$A121,'S1'!$E$6:$E$32,"Diego")+COUNTIFS('S1'!$B$6:$B$32,$A121,'S1'!$E$6:$E$32,"Ambos")+COUNTIFS('S2'!$B$6:$B$23,$A121,'S2'!$E$6:$E$23,"Diego")+COUNTIFS('S2'!$B$6:$B$23,$A121,'S2'!$E$6:$E$23,"Ambos")+COUNTIFS('S3'!$B$6:$B$24,$A121,'S3'!$E$6:$E$24,"Diego")+COUNTIFS('S3'!$B$6:$B$24,$A121,'S3'!$E$6:$E$24,"Ambos")+COUNTIFS('S4'!$B$6:$B$22,$A121,'S4'!$E$6:$E$22,"Diego")+COUNTIFS('S4'!$B$6:$B$22,$A121,'S4'!$E$6:$E$22,"Ambos")+COUNTIFS('S5'!$B$6:$B$20,$A121,'S5'!$E$6:$E$20,"Diego")+COUNTIFS('S5'!$B$6:$B$20,$A121,'S5'!$E$6:$E$20,"Ambos")+COUNTIFS('S6'!$B$6:$B$17,$A121,'S6'!$E$6:$E$17,"Diego")+COUNTIFS('S6'!$B$6:$B$17,$A121,'S6'!$E$6:$E$17,"Ambos")+COUNTIFS('S7'!$B$6:$B$19,$A121,'S7'!$E$6:$E$19,"Diego")+COUNTIFS('S7'!$B$6:$B$19,$A121,'S7'!$E$6:$E$19,"Ambos")+COUNTIFS('S8'!$B$6:$B$23,$A121,'S8'!$E$6:$E$23,"Diego")+COUNTIFS('S8'!$B$6:$B$23,$A121,'S8'!$E$6:$E$23,"Ambos")+COUNTIFS('S9'!$B$6:$B$15,$A121,'S9'!$E$6:$E$15,"Diego")+COUNTIFS('S9'!$B$6:$B$15,$A121,'S9'!$E$6:$E$15,"Ambos")+COUNTIFS('S10'!$B$6:$B$13,$A121,'S10'!$E$6:$E$13,"Diego")+COUNTIFS('S10'!$B$6:$B$13,$A121,'S10'!$E$6:$E$13,"Ambos")+COUNTIFS('Holgura'!$B$6:$B$11,$A121,'Holgura'!$E$6:$E$11,"Diego")+COUNTIFS('Holgura'!$B$6:$B$11,$A121,'Holgura'!$E$6:$E$11,"Ambos")+COUNTIFS('Entrega'!$B$6:$B$9,$A121,'Entrega'!$E$6:$E$9,"Diego")+COUNTIFS('Entrega'!$B$6:$B$9,$A121,'Entrega'!$E$6:$E$9,"Ambos")+COUNTIFS('Defensa'!$B$6:$B$10,$A121,'Defensa'!$E$6:$E$10,"Diego")+COUNTIFS('Defensa'!$B$6:$B$10,$A121,'Defensa'!$E$6:$E$10,"Ambos")</f>
         <v/>
       </c>
     </row>
@@ -12073,19 +12094,19 @@
         <v/>
       </c>
       <c r="D122" s="21">
-        <f>SUMIFS('S1'!$I$6:$I$32,'S1'!$B$6:$B$32,$A122,'S1'!$E$6:$E$32,"Víctor")+SUMIFS('S1'!$I$6:$I$32,'S1'!$B$6:$B$32,$A122,'S1'!$E$6:$E$32,"Ambos")+SUMIFS('S2'!$I$6:$I$23,'S2'!$B$6:$B$23,$A122,'S2'!$E$6:$E$23,"Víctor")+SUMIFS('S2'!$I$6:$I$23,'S2'!$B$6:$B$23,$A122,'S2'!$E$6:$E$23,"Ambos")+SUMIFS('S3'!$I$6:$I$19,'S3'!$B$6:$B$19,$A122,'S3'!$E$6:$E$19,"Víctor")+SUMIFS('S3'!$I$6:$I$19,'S3'!$B$6:$B$19,$A122,'S3'!$E$6:$E$19,"Ambos")+SUMIFS('S4'!$I$6:$I$20,'S4'!$B$6:$B$20,$A122,'S4'!$E$6:$E$20,"Víctor")+SUMIFS('S4'!$I$6:$I$20,'S4'!$B$6:$B$20,$A122,'S4'!$E$6:$E$20,"Ambos")+SUMIFS('S5'!$I$6:$I$20,'S5'!$B$6:$B$20,$A122,'S5'!$E$6:$E$20,"Víctor")+SUMIFS('S5'!$I$6:$I$20,'S5'!$B$6:$B$20,$A122,'S5'!$E$6:$E$20,"Ambos")+SUMIFS('S6'!$I$6:$I$17,'S6'!$B$6:$B$17,$A122,'S6'!$E$6:$E$17,"Víctor")+SUMIFS('S6'!$I$6:$I$17,'S6'!$B$6:$B$17,$A122,'S6'!$E$6:$E$17,"Ambos")+SUMIFS('S7'!$I$6:$I$19,'S7'!$B$6:$B$19,$A122,'S7'!$E$6:$E$19,"Víctor")+SUMIFS('S7'!$I$6:$I$19,'S7'!$B$6:$B$19,$A122,'S7'!$E$6:$E$19,"Ambos")+SUMIFS('S8'!$I$6:$I$23,'S8'!$B$6:$B$23,$A122,'S8'!$E$6:$E$23,"Víctor")+SUMIFS('S8'!$I$6:$I$23,'S8'!$B$6:$B$23,$A122,'S8'!$E$6:$E$23,"Ambos")+SUMIFS('S9'!$I$6:$I$15,'S9'!$B$6:$B$15,$A122,'S9'!$E$6:$E$15,"Víctor")+SUMIFS('S9'!$I$6:$I$15,'S9'!$B$6:$B$15,$A122,'S9'!$E$6:$E$15,"Ambos")+SUMIFS('S10'!$I$6:$I$13,'S10'!$B$6:$B$13,$A122,'S10'!$E$6:$E$13,"Víctor")+SUMIFS('S10'!$I$6:$I$13,'S10'!$B$6:$B$13,$A122,'S10'!$E$6:$E$13,"Ambos")+SUMIFS('Holgura'!$I$6:$I$11,'Holgura'!$B$6:$B$11,$A122,'Holgura'!$E$6:$E$11,"Víctor")+SUMIFS('Holgura'!$I$6:$I$11,'Holgura'!$B$6:$B$11,$A122,'Holgura'!$E$6:$E$11,"Ambos")+SUMIFS('Entrega'!$I$6:$I$9,'Entrega'!$B$6:$B$9,$A122,'Entrega'!$E$6:$E$9,"Víctor")+SUMIFS('Entrega'!$I$6:$I$9,'Entrega'!$B$6:$B$9,$A122,'Entrega'!$E$6:$E$9,"Ambos")+SUMIFS('Defensa'!$I$6:$I$10,'Defensa'!$B$6:$B$10,$A122,'Defensa'!$E$6:$E$10,"Víctor")+SUMIFS('Defensa'!$I$6:$I$10,'Defensa'!$B$6:$B$10,$A122,'Defensa'!$E$6:$E$10,"Ambos")</f>
+        <f>SUMIFS('S1'!$I$6:$I$32,'S1'!$B$6:$B$32,$A122,'S1'!$E$6:$E$32,"Víctor")+SUMIFS('S1'!$I$6:$I$32,'S1'!$B$6:$B$32,$A122,'S1'!$E$6:$E$32,"Ambos")+SUMIFS('S2'!$I$6:$I$23,'S2'!$B$6:$B$23,$A122,'S2'!$E$6:$E$23,"Víctor")+SUMIFS('S2'!$I$6:$I$23,'S2'!$B$6:$B$23,$A122,'S2'!$E$6:$E$23,"Ambos")+SUMIFS('S3'!$I$6:$I$24,'S3'!$B$6:$B$24,$A122,'S3'!$E$6:$E$24,"Víctor")+SUMIFS('S3'!$I$6:$I$24,'S3'!$B$6:$B$24,$A122,'S3'!$E$6:$E$24,"Ambos")+SUMIFS('S4'!$I$6:$I$22,'S4'!$B$6:$B$22,$A122,'S4'!$E$6:$E$22,"Víctor")+SUMIFS('S4'!$I$6:$I$22,'S4'!$B$6:$B$22,$A122,'S4'!$E$6:$E$22,"Ambos")+SUMIFS('S5'!$I$6:$I$20,'S5'!$B$6:$B$20,$A122,'S5'!$E$6:$E$20,"Víctor")+SUMIFS('S5'!$I$6:$I$20,'S5'!$B$6:$B$20,$A122,'S5'!$E$6:$E$20,"Ambos")+SUMIFS('S6'!$I$6:$I$17,'S6'!$B$6:$B$17,$A122,'S6'!$E$6:$E$17,"Víctor")+SUMIFS('S6'!$I$6:$I$17,'S6'!$B$6:$B$17,$A122,'S6'!$E$6:$E$17,"Ambos")+SUMIFS('S7'!$I$6:$I$19,'S7'!$B$6:$B$19,$A122,'S7'!$E$6:$E$19,"Víctor")+SUMIFS('S7'!$I$6:$I$19,'S7'!$B$6:$B$19,$A122,'S7'!$E$6:$E$19,"Ambos")+SUMIFS('S8'!$I$6:$I$23,'S8'!$B$6:$B$23,$A122,'S8'!$E$6:$E$23,"Víctor")+SUMIFS('S8'!$I$6:$I$23,'S8'!$B$6:$B$23,$A122,'S8'!$E$6:$E$23,"Ambos")+SUMIFS('S9'!$I$6:$I$15,'S9'!$B$6:$B$15,$A122,'S9'!$E$6:$E$15,"Víctor")+SUMIFS('S9'!$I$6:$I$15,'S9'!$B$6:$B$15,$A122,'S9'!$E$6:$E$15,"Ambos")+SUMIFS('S10'!$I$6:$I$13,'S10'!$B$6:$B$13,$A122,'S10'!$E$6:$E$13,"Víctor")+SUMIFS('S10'!$I$6:$I$13,'S10'!$B$6:$B$13,$A122,'S10'!$E$6:$E$13,"Ambos")+SUMIFS('Holgura'!$I$6:$I$11,'Holgura'!$B$6:$B$11,$A122,'Holgura'!$E$6:$E$11,"Víctor")+SUMIFS('Holgura'!$I$6:$I$11,'Holgura'!$B$6:$B$11,$A122,'Holgura'!$E$6:$E$11,"Ambos")+SUMIFS('Entrega'!$I$6:$I$9,'Entrega'!$B$6:$B$9,$A122,'Entrega'!$E$6:$E$9,"Víctor")+SUMIFS('Entrega'!$I$6:$I$9,'Entrega'!$B$6:$B$9,$A122,'Entrega'!$E$6:$E$9,"Ambos")+SUMIFS('Defensa'!$I$6:$I$10,'Defensa'!$B$6:$B$10,$A122,'Defensa'!$E$6:$E$10,"Víctor")+SUMIFS('Defensa'!$I$6:$I$10,'Defensa'!$B$6:$B$10,$A122,'Defensa'!$E$6:$E$10,"Ambos")</f>
         <v/>
       </c>
       <c r="E122" s="21">
-        <f>SUMIFS('S1'!$I$6:$I$32,'S1'!$B$6:$B$32,$A122,'S1'!$E$6:$E$32,"Diego")+SUMIFS('S1'!$I$6:$I$32,'S1'!$B$6:$B$32,$A122,'S1'!$E$6:$E$32,"Ambos")+SUMIFS('S2'!$I$6:$I$23,'S2'!$B$6:$B$23,$A122,'S2'!$E$6:$E$23,"Diego")+SUMIFS('S2'!$I$6:$I$23,'S2'!$B$6:$B$23,$A122,'S2'!$E$6:$E$23,"Ambos")+SUMIFS('S3'!$I$6:$I$19,'S3'!$B$6:$B$19,$A122,'S3'!$E$6:$E$19,"Diego")+SUMIFS('S3'!$I$6:$I$19,'S3'!$B$6:$B$19,$A122,'S3'!$E$6:$E$19,"Ambos")+SUMIFS('S4'!$I$6:$I$20,'S4'!$B$6:$B$20,$A122,'S4'!$E$6:$E$20,"Diego")+SUMIFS('S4'!$I$6:$I$20,'S4'!$B$6:$B$20,$A122,'S4'!$E$6:$E$20,"Ambos")+SUMIFS('S5'!$I$6:$I$20,'S5'!$B$6:$B$20,$A122,'S5'!$E$6:$E$20,"Diego")+SUMIFS('S5'!$I$6:$I$20,'S5'!$B$6:$B$20,$A122,'S5'!$E$6:$E$20,"Ambos")+SUMIFS('S6'!$I$6:$I$17,'S6'!$B$6:$B$17,$A122,'S6'!$E$6:$E$17,"Diego")+SUMIFS('S6'!$I$6:$I$17,'S6'!$B$6:$B$17,$A122,'S6'!$E$6:$E$17,"Ambos")+SUMIFS('S7'!$I$6:$I$19,'S7'!$B$6:$B$19,$A122,'S7'!$E$6:$E$19,"Diego")+SUMIFS('S7'!$I$6:$I$19,'S7'!$B$6:$B$19,$A122,'S7'!$E$6:$E$19,"Ambos")+SUMIFS('S8'!$I$6:$I$23,'S8'!$B$6:$B$23,$A122,'S8'!$E$6:$E$23,"Diego")+SUMIFS('S8'!$I$6:$I$23,'S8'!$B$6:$B$23,$A122,'S8'!$E$6:$E$23,"Ambos")+SUMIFS('S9'!$I$6:$I$15,'S9'!$B$6:$B$15,$A122,'S9'!$E$6:$E$15,"Diego")+SUMIFS('S9'!$I$6:$I$15,'S9'!$B$6:$B$15,$A122,'S9'!$E$6:$E$15,"Ambos")+SUMIFS('S10'!$I$6:$I$13,'S10'!$B$6:$B$13,$A122,'S10'!$E$6:$E$13,"Diego")+SUMIFS('S10'!$I$6:$I$13,'S10'!$B$6:$B$13,$A122,'S10'!$E$6:$E$13,"Ambos")+SUMIFS('Holgura'!$I$6:$I$11,'Holgura'!$B$6:$B$11,$A122,'Holgura'!$E$6:$E$11,"Diego")+SUMIFS('Holgura'!$I$6:$I$11,'Holgura'!$B$6:$B$11,$A122,'Holgura'!$E$6:$E$11,"Ambos")+SUMIFS('Entrega'!$I$6:$I$9,'Entrega'!$B$6:$B$9,$A122,'Entrega'!$E$6:$E$9,"Diego")+SUMIFS('Entrega'!$I$6:$I$9,'Entrega'!$B$6:$B$9,$A122,'Entrega'!$E$6:$E$9,"Ambos")+SUMIFS('Defensa'!$I$6:$I$10,'Defensa'!$B$6:$B$10,$A122,'Defensa'!$E$6:$E$10,"Diego")+SUMIFS('Defensa'!$I$6:$I$10,'Defensa'!$B$6:$B$10,$A122,'Defensa'!$E$6:$E$10,"Ambos")</f>
+        <f>SUMIFS('S1'!$I$6:$I$32,'S1'!$B$6:$B$32,$A122,'S1'!$E$6:$E$32,"Diego")+SUMIFS('S1'!$I$6:$I$32,'S1'!$B$6:$B$32,$A122,'S1'!$E$6:$E$32,"Ambos")+SUMIFS('S2'!$I$6:$I$23,'S2'!$B$6:$B$23,$A122,'S2'!$E$6:$E$23,"Diego")+SUMIFS('S2'!$I$6:$I$23,'S2'!$B$6:$B$23,$A122,'S2'!$E$6:$E$23,"Ambos")+SUMIFS('S3'!$I$6:$I$24,'S3'!$B$6:$B$24,$A122,'S3'!$E$6:$E$24,"Diego")+SUMIFS('S3'!$I$6:$I$24,'S3'!$B$6:$B$24,$A122,'S3'!$E$6:$E$24,"Ambos")+SUMIFS('S4'!$I$6:$I$22,'S4'!$B$6:$B$22,$A122,'S4'!$E$6:$E$22,"Diego")+SUMIFS('S4'!$I$6:$I$22,'S4'!$B$6:$B$22,$A122,'S4'!$E$6:$E$22,"Ambos")+SUMIFS('S5'!$I$6:$I$20,'S5'!$B$6:$B$20,$A122,'S5'!$E$6:$E$20,"Diego")+SUMIFS('S5'!$I$6:$I$20,'S5'!$B$6:$B$20,$A122,'S5'!$E$6:$E$20,"Ambos")+SUMIFS('S6'!$I$6:$I$17,'S6'!$B$6:$B$17,$A122,'S6'!$E$6:$E$17,"Diego")+SUMIFS('S6'!$I$6:$I$17,'S6'!$B$6:$B$17,$A122,'S6'!$E$6:$E$17,"Ambos")+SUMIFS('S7'!$I$6:$I$19,'S7'!$B$6:$B$19,$A122,'S7'!$E$6:$E$19,"Diego")+SUMIFS('S7'!$I$6:$I$19,'S7'!$B$6:$B$19,$A122,'S7'!$E$6:$E$19,"Ambos")+SUMIFS('S8'!$I$6:$I$23,'S8'!$B$6:$B$23,$A122,'S8'!$E$6:$E$23,"Diego")+SUMIFS('S8'!$I$6:$I$23,'S8'!$B$6:$B$23,$A122,'S8'!$E$6:$E$23,"Ambos")+SUMIFS('S9'!$I$6:$I$15,'S9'!$B$6:$B$15,$A122,'S9'!$E$6:$E$15,"Diego")+SUMIFS('S9'!$I$6:$I$15,'S9'!$B$6:$B$15,$A122,'S9'!$E$6:$E$15,"Ambos")+SUMIFS('S10'!$I$6:$I$13,'S10'!$B$6:$B$13,$A122,'S10'!$E$6:$E$13,"Diego")+SUMIFS('S10'!$I$6:$I$13,'S10'!$B$6:$B$13,$A122,'S10'!$E$6:$E$13,"Ambos")+SUMIFS('Holgura'!$I$6:$I$11,'Holgura'!$B$6:$B$11,$A122,'Holgura'!$E$6:$E$11,"Diego")+SUMIFS('Holgura'!$I$6:$I$11,'Holgura'!$B$6:$B$11,$A122,'Holgura'!$E$6:$E$11,"Ambos")+SUMIFS('Entrega'!$I$6:$I$9,'Entrega'!$B$6:$B$9,$A122,'Entrega'!$E$6:$E$9,"Diego")+SUMIFS('Entrega'!$I$6:$I$9,'Entrega'!$B$6:$B$9,$A122,'Entrega'!$E$6:$E$9,"Ambos")+SUMIFS('Defensa'!$I$6:$I$10,'Defensa'!$B$6:$B$10,$A122,'Defensa'!$E$6:$E$10,"Diego")+SUMIFS('Defensa'!$I$6:$I$10,'Defensa'!$B$6:$B$10,$A122,'Defensa'!$E$6:$E$10,"Ambos")</f>
         <v/>
       </c>
       <c r="F122" s="21">
-        <f>COUNTIFS('S1'!$B$6:$B$32,$A122,'S1'!$E$6:$E$32,"Víctor")+COUNTIFS('S1'!$B$6:$B$32,$A122,'S1'!$E$6:$E$32,"Ambos")+COUNTIFS('S2'!$B$6:$B$23,$A122,'S2'!$E$6:$E$23,"Víctor")+COUNTIFS('S2'!$B$6:$B$23,$A122,'S2'!$E$6:$E$23,"Ambos")+COUNTIFS('S3'!$B$6:$B$19,$A122,'S3'!$E$6:$E$19,"Víctor")+COUNTIFS('S3'!$B$6:$B$19,$A122,'S3'!$E$6:$E$19,"Ambos")+COUNTIFS('S4'!$B$6:$B$20,$A122,'S4'!$E$6:$E$20,"Víctor")+COUNTIFS('S4'!$B$6:$B$20,$A122,'S4'!$E$6:$E$20,"Ambos")+COUNTIFS('S5'!$B$6:$B$20,$A122,'S5'!$E$6:$E$20,"Víctor")+COUNTIFS('S5'!$B$6:$B$20,$A122,'S5'!$E$6:$E$20,"Ambos")+COUNTIFS('S6'!$B$6:$B$17,$A122,'S6'!$E$6:$E$17,"Víctor")+COUNTIFS('S6'!$B$6:$B$17,$A122,'S6'!$E$6:$E$17,"Ambos")+COUNTIFS('S7'!$B$6:$B$19,$A122,'S7'!$E$6:$E$19,"Víctor")+COUNTIFS('S7'!$B$6:$B$19,$A122,'S7'!$E$6:$E$19,"Ambos")+COUNTIFS('S8'!$B$6:$B$23,$A122,'S8'!$E$6:$E$23,"Víctor")+COUNTIFS('S8'!$B$6:$B$23,$A122,'S8'!$E$6:$E$23,"Ambos")+COUNTIFS('S9'!$B$6:$B$15,$A122,'S9'!$E$6:$E$15,"Víctor")+COUNTIFS('S9'!$B$6:$B$15,$A122,'S9'!$E$6:$E$15,"Ambos")+COUNTIFS('S10'!$B$6:$B$13,$A122,'S10'!$E$6:$E$13,"Víctor")+COUNTIFS('S10'!$B$6:$B$13,$A122,'S10'!$E$6:$E$13,"Ambos")+COUNTIFS('Holgura'!$B$6:$B$11,$A122,'Holgura'!$E$6:$E$11,"Víctor")+COUNTIFS('Holgura'!$B$6:$B$11,$A122,'Holgura'!$E$6:$E$11,"Ambos")+COUNTIFS('Entrega'!$B$6:$B$9,$A122,'Entrega'!$E$6:$E$9,"Víctor")+COUNTIFS('Entrega'!$B$6:$B$9,$A122,'Entrega'!$E$6:$E$9,"Ambos")+COUNTIFS('Defensa'!$B$6:$B$10,$A122,'Defensa'!$E$6:$E$10,"Víctor")+COUNTIFS('Defensa'!$B$6:$B$10,$A122,'Defensa'!$E$6:$E$10,"Ambos")</f>
+        <f>COUNTIFS('S1'!$B$6:$B$32,$A122,'S1'!$E$6:$E$32,"Víctor")+COUNTIFS('S1'!$B$6:$B$32,$A122,'S1'!$E$6:$E$32,"Ambos")+COUNTIFS('S2'!$B$6:$B$23,$A122,'S2'!$E$6:$E$23,"Víctor")+COUNTIFS('S2'!$B$6:$B$23,$A122,'S2'!$E$6:$E$23,"Ambos")+COUNTIFS('S3'!$B$6:$B$24,$A122,'S3'!$E$6:$E$24,"Víctor")+COUNTIFS('S3'!$B$6:$B$24,$A122,'S3'!$E$6:$E$24,"Ambos")+COUNTIFS('S4'!$B$6:$B$22,$A122,'S4'!$E$6:$E$22,"Víctor")+COUNTIFS('S4'!$B$6:$B$22,$A122,'S4'!$E$6:$E$22,"Ambos")+COUNTIFS('S5'!$B$6:$B$20,$A122,'S5'!$E$6:$E$20,"Víctor")+COUNTIFS('S5'!$B$6:$B$20,$A122,'S5'!$E$6:$E$20,"Ambos")+COUNTIFS('S6'!$B$6:$B$17,$A122,'S6'!$E$6:$E$17,"Víctor")+COUNTIFS('S6'!$B$6:$B$17,$A122,'S6'!$E$6:$E$17,"Ambos")+COUNTIFS('S7'!$B$6:$B$19,$A122,'S7'!$E$6:$E$19,"Víctor")+COUNTIFS('S7'!$B$6:$B$19,$A122,'S7'!$E$6:$E$19,"Ambos")+COUNTIFS('S8'!$B$6:$B$23,$A122,'S8'!$E$6:$E$23,"Víctor")+COUNTIFS('S8'!$B$6:$B$23,$A122,'S8'!$E$6:$E$23,"Ambos")+COUNTIFS('S9'!$B$6:$B$15,$A122,'S9'!$E$6:$E$15,"Víctor")+COUNTIFS('S9'!$B$6:$B$15,$A122,'S9'!$E$6:$E$15,"Ambos")+COUNTIFS('S10'!$B$6:$B$13,$A122,'S10'!$E$6:$E$13,"Víctor")+COUNTIFS('S10'!$B$6:$B$13,$A122,'S10'!$E$6:$E$13,"Ambos")+COUNTIFS('Holgura'!$B$6:$B$11,$A122,'Holgura'!$E$6:$E$11,"Víctor")+COUNTIFS('Holgura'!$B$6:$B$11,$A122,'Holgura'!$E$6:$E$11,"Ambos")+COUNTIFS('Entrega'!$B$6:$B$9,$A122,'Entrega'!$E$6:$E$9,"Víctor")+COUNTIFS('Entrega'!$B$6:$B$9,$A122,'Entrega'!$E$6:$E$9,"Ambos")+COUNTIFS('Defensa'!$B$6:$B$10,$A122,'Defensa'!$E$6:$E$10,"Víctor")+COUNTIFS('Defensa'!$B$6:$B$10,$A122,'Defensa'!$E$6:$E$10,"Ambos")</f>
         <v/>
       </c>
       <c r="G122" s="21">
-        <f>COUNTIFS('S1'!$B$6:$B$32,$A122,'S1'!$E$6:$E$32,"Diego")+COUNTIFS('S1'!$B$6:$B$32,$A122,'S1'!$E$6:$E$32,"Ambos")+COUNTIFS('S2'!$B$6:$B$23,$A122,'S2'!$E$6:$E$23,"Diego")+COUNTIFS('S2'!$B$6:$B$23,$A122,'S2'!$E$6:$E$23,"Ambos")+COUNTIFS('S3'!$B$6:$B$19,$A122,'S3'!$E$6:$E$19,"Diego")+COUNTIFS('S3'!$B$6:$B$19,$A122,'S3'!$E$6:$E$19,"Ambos")+COUNTIFS('S4'!$B$6:$B$20,$A122,'S4'!$E$6:$E$20,"Diego")+COUNTIFS('S4'!$B$6:$B$20,$A122,'S4'!$E$6:$E$20,"Ambos")+COUNTIFS('S5'!$B$6:$B$20,$A122,'S5'!$E$6:$E$20,"Diego")+COUNTIFS('S5'!$B$6:$B$20,$A122,'S5'!$E$6:$E$20,"Ambos")+COUNTIFS('S6'!$B$6:$B$17,$A122,'S6'!$E$6:$E$17,"Diego")+COUNTIFS('S6'!$B$6:$B$17,$A122,'S6'!$E$6:$E$17,"Ambos")+COUNTIFS('S7'!$B$6:$B$19,$A122,'S7'!$E$6:$E$19,"Diego")+COUNTIFS('S7'!$B$6:$B$19,$A122,'S7'!$E$6:$E$19,"Ambos")+COUNTIFS('S8'!$B$6:$B$23,$A122,'S8'!$E$6:$E$23,"Diego")+COUNTIFS('S8'!$B$6:$B$23,$A122,'S8'!$E$6:$E$23,"Ambos")+COUNTIFS('S9'!$B$6:$B$15,$A122,'S9'!$E$6:$E$15,"Diego")+COUNTIFS('S9'!$B$6:$B$15,$A122,'S9'!$E$6:$E$15,"Ambos")+COUNTIFS('S10'!$B$6:$B$13,$A122,'S10'!$E$6:$E$13,"Diego")+COUNTIFS('S10'!$B$6:$B$13,$A122,'S10'!$E$6:$E$13,"Ambos")+COUNTIFS('Holgura'!$B$6:$B$11,$A122,'Holgura'!$E$6:$E$11,"Diego")+COUNTIFS('Holgura'!$B$6:$B$11,$A122,'Holgura'!$E$6:$E$11,"Ambos")+COUNTIFS('Entrega'!$B$6:$B$9,$A122,'Entrega'!$E$6:$E$9,"Diego")+COUNTIFS('Entrega'!$B$6:$B$9,$A122,'Entrega'!$E$6:$E$9,"Ambos")+COUNTIFS('Defensa'!$B$6:$B$10,$A122,'Defensa'!$E$6:$E$10,"Diego")+COUNTIFS('Defensa'!$B$6:$B$10,$A122,'Defensa'!$E$6:$E$10,"Ambos")</f>
+        <f>COUNTIFS('S1'!$B$6:$B$32,$A122,'S1'!$E$6:$E$32,"Diego")+COUNTIFS('S1'!$B$6:$B$32,$A122,'S1'!$E$6:$E$32,"Ambos")+COUNTIFS('S2'!$B$6:$B$23,$A122,'S2'!$E$6:$E$23,"Diego")+COUNTIFS('S2'!$B$6:$B$23,$A122,'S2'!$E$6:$E$23,"Ambos")+COUNTIFS('S3'!$B$6:$B$24,$A122,'S3'!$E$6:$E$24,"Diego")+COUNTIFS('S3'!$B$6:$B$24,$A122,'S3'!$E$6:$E$24,"Ambos")+COUNTIFS('S4'!$B$6:$B$22,$A122,'S4'!$E$6:$E$22,"Diego")+COUNTIFS('S4'!$B$6:$B$22,$A122,'S4'!$E$6:$E$22,"Ambos")+COUNTIFS('S5'!$B$6:$B$20,$A122,'S5'!$E$6:$E$20,"Diego")+COUNTIFS('S5'!$B$6:$B$20,$A122,'S5'!$E$6:$E$20,"Ambos")+COUNTIFS('S6'!$B$6:$B$17,$A122,'S6'!$E$6:$E$17,"Diego")+COUNTIFS('S6'!$B$6:$B$17,$A122,'S6'!$E$6:$E$17,"Ambos")+COUNTIFS('S7'!$B$6:$B$19,$A122,'S7'!$E$6:$E$19,"Diego")+COUNTIFS('S7'!$B$6:$B$19,$A122,'S7'!$E$6:$E$19,"Ambos")+COUNTIFS('S8'!$B$6:$B$23,$A122,'S8'!$E$6:$E$23,"Diego")+COUNTIFS('S8'!$B$6:$B$23,$A122,'S8'!$E$6:$E$23,"Ambos")+COUNTIFS('S9'!$B$6:$B$15,$A122,'S9'!$E$6:$E$15,"Diego")+COUNTIFS('S9'!$B$6:$B$15,$A122,'S9'!$E$6:$E$15,"Ambos")+COUNTIFS('S10'!$B$6:$B$13,$A122,'S10'!$E$6:$E$13,"Diego")+COUNTIFS('S10'!$B$6:$B$13,$A122,'S10'!$E$6:$E$13,"Ambos")+COUNTIFS('Holgura'!$B$6:$B$11,$A122,'Holgura'!$E$6:$E$11,"Diego")+COUNTIFS('Holgura'!$B$6:$B$11,$A122,'Holgura'!$E$6:$E$11,"Ambos")+COUNTIFS('Entrega'!$B$6:$B$9,$A122,'Entrega'!$E$6:$E$9,"Diego")+COUNTIFS('Entrega'!$B$6:$B$9,$A122,'Entrega'!$E$6:$E$9,"Ambos")+COUNTIFS('Defensa'!$B$6:$B$10,$A122,'Defensa'!$E$6:$E$10,"Diego")+COUNTIFS('Defensa'!$B$6:$B$10,$A122,'Defensa'!$E$6:$E$10,"Ambos")</f>
         <v/>
       </c>
     </row>
@@ -12102,19 +12123,19 @@
         <v/>
       </c>
       <c r="D123" s="21">
-        <f>SUMIFS('S1'!$I$6:$I$32,'S1'!$B$6:$B$32,$A123,'S1'!$E$6:$E$32,"Víctor")+SUMIFS('S1'!$I$6:$I$32,'S1'!$B$6:$B$32,$A123,'S1'!$E$6:$E$32,"Ambos")+SUMIFS('S2'!$I$6:$I$23,'S2'!$B$6:$B$23,$A123,'S2'!$E$6:$E$23,"Víctor")+SUMIFS('S2'!$I$6:$I$23,'S2'!$B$6:$B$23,$A123,'S2'!$E$6:$E$23,"Ambos")+SUMIFS('S3'!$I$6:$I$19,'S3'!$B$6:$B$19,$A123,'S3'!$E$6:$E$19,"Víctor")+SUMIFS('S3'!$I$6:$I$19,'S3'!$B$6:$B$19,$A123,'S3'!$E$6:$E$19,"Ambos")+SUMIFS('S4'!$I$6:$I$20,'S4'!$B$6:$B$20,$A123,'S4'!$E$6:$E$20,"Víctor")+SUMIFS('S4'!$I$6:$I$20,'S4'!$B$6:$B$20,$A123,'S4'!$E$6:$E$20,"Ambos")+SUMIFS('S5'!$I$6:$I$20,'S5'!$B$6:$B$20,$A123,'S5'!$E$6:$E$20,"Víctor")+SUMIFS('S5'!$I$6:$I$20,'S5'!$B$6:$B$20,$A123,'S5'!$E$6:$E$20,"Ambos")+SUMIFS('S6'!$I$6:$I$17,'S6'!$B$6:$B$17,$A123,'S6'!$E$6:$E$17,"Víctor")+SUMIFS('S6'!$I$6:$I$17,'S6'!$B$6:$B$17,$A123,'S6'!$E$6:$E$17,"Ambos")+SUMIFS('S7'!$I$6:$I$19,'S7'!$B$6:$B$19,$A123,'S7'!$E$6:$E$19,"Víctor")+SUMIFS('S7'!$I$6:$I$19,'S7'!$B$6:$B$19,$A123,'S7'!$E$6:$E$19,"Ambos")+SUMIFS('S8'!$I$6:$I$23,'S8'!$B$6:$B$23,$A123,'S8'!$E$6:$E$23,"Víctor")+SUMIFS('S8'!$I$6:$I$23,'S8'!$B$6:$B$23,$A123,'S8'!$E$6:$E$23,"Ambos")+SUMIFS('S9'!$I$6:$I$15,'S9'!$B$6:$B$15,$A123,'S9'!$E$6:$E$15,"Víctor")+SUMIFS('S9'!$I$6:$I$15,'S9'!$B$6:$B$15,$A123,'S9'!$E$6:$E$15,"Ambos")+SUMIFS('S10'!$I$6:$I$13,'S10'!$B$6:$B$13,$A123,'S10'!$E$6:$E$13,"Víctor")+SUMIFS('S10'!$I$6:$I$13,'S10'!$B$6:$B$13,$A123,'S10'!$E$6:$E$13,"Ambos")+SUMIFS('Holgura'!$I$6:$I$11,'Holgura'!$B$6:$B$11,$A123,'Holgura'!$E$6:$E$11,"Víctor")+SUMIFS('Holgura'!$I$6:$I$11,'Holgura'!$B$6:$B$11,$A123,'Holgura'!$E$6:$E$11,"Ambos")+SUMIFS('Entrega'!$I$6:$I$9,'Entrega'!$B$6:$B$9,$A123,'Entrega'!$E$6:$E$9,"Víctor")+SUMIFS('Entrega'!$I$6:$I$9,'Entrega'!$B$6:$B$9,$A123,'Entrega'!$E$6:$E$9,"Ambos")+SUMIFS('Defensa'!$I$6:$I$10,'Defensa'!$B$6:$B$10,$A123,'Defensa'!$E$6:$E$10,"Víctor")+SUMIFS('Defensa'!$I$6:$I$10,'Defensa'!$B$6:$B$10,$A123,'Defensa'!$E$6:$E$10,"Ambos")</f>
+        <f>SUMIFS('S1'!$I$6:$I$32,'S1'!$B$6:$B$32,$A123,'S1'!$E$6:$E$32,"Víctor")+SUMIFS('S1'!$I$6:$I$32,'S1'!$B$6:$B$32,$A123,'S1'!$E$6:$E$32,"Ambos")+SUMIFS('S2'!$I$6:$I$23,'S2'!$B$6:$B$23,$A123,'S2'!$E$6:$E$23,"Víctor")+SUMIFS('S2'!$I$6:$I$23,'S2'!$B$6:$B$23,$A123,'S2'!$E$6:$E$23,"Ambos")+SUMIFS('S3'!$I$6:$I$24,'S3'!$B$6:$B$24,$A123,'S3'!$E$6:$E$24,"Víctor")+SUMIFS('S3'!$I$6:$I$24,'S3'!$B$6:$B$24,$A123,'S3'!$E$6:$E$24,"Ambos")+SUMIFS('S4'!$I$6:$I$22,'S4'!$B$6:$B$22,$A123,'S4'!$E$6:$E$22,"Víctor")+SUMIFS('S4'!$I$6:$I$22,'S4'!$B$6:$B$22,$A123,'S4'!$E$6:$E$22,"Ambos")+SUMIFS('S5'!$I$6:$I$20,'S5'!$B$6:$B$20,$A123,'S5'!$E$6:$E$20,"Víctor")+SUMIFS('S5'!$I$6:$I$20,'S5'!$B$6:$B$20,$A123,'S5'!$E$6:$E$20,"Ambos")+SUMIFS('S6'!$I$6:$I$17,'S6'!$B$6:$B$17,$A123,'S6'!$E$6:$E$17,"Víctor")+SUMIFS('S6'!$I$6:$I$17,'S6'!$B$6:$B$17,$A123,'S6'!$E$6:$E$17,"Ambos")+SUMIFS('S7'!$I$6:$I$19,'S7'!$B$6:$B$19,$A123,'S7'!$E$6:$E$19,"Víctor")+SUMIFS('S7'!$I$6:$I$19,'S7'!$B$6:$B$19,$A123,'S7'!$E$6:$E$19,"Ambos")+SUMIFS('S8'!$I$6:$I$23,'S8'!$B$6:$B$23,$A123,'S8'!$E$6:$E$23,"Víctor")+SUMIFS('S8'!$I$6:$I$23,'S8'!$B$6:$B$23,$A123,'S8'!$E$6:$E$23,"Ambos")+SUMIFS('S9'!$I$6:$I$15,'S9'!$B$6:$B$15,$A123,'S9'!$E$6:$E$15,"Víctor")+SUMIFS('S9'!$I$6:$I$15,'S9'!$B$6:$B$15,$A123,'S9'!$E$6:$E$15,"Ambos")+SUMIFS('S10'!$I$6:$I$13,'S10'!$B$6:$B$13,$A123,'S10'!$E$6:$E$13,"Víctor")+SUMIFS('S10'!$I$6:$I$13,'S10'!$B$6:$B$13,$A123,'S10'!$E$6:$E$13,"Ambos")+SUMIFS('Holgura'!$I$6:$I$11,'Holgura'!$B$6:$B$11,$A123,'Holgura'!$E$6:$E$11,"Víctor")+SUMIFS('Holgura'!$I$6:$I$11,'Holgura'!$B$6:$B$11,$A123,'Holgura'!$E$6:$E$11,"Ambos")+SUMIFS('Entrega'!$I$6:$I$9,'Entrega'!$B$6:$B$9,$A123,'Entrega'!$E$6:$E$9,"Víctor")+SUMIFS('Entrega'!$I$6:$I$9,'Entrega'!$B$6:$B$9,$A123,'Entrega'!$E$6:$E$9,"Ambos")+SUMIFS('Defensa'!$I$6:$I$10,'Defensa'!$B$6:$B$10,$A123,'Defensa'!$E$6:$E$10,"Víctor")+SUMIFS('Defensa'!$I$6:$I$10,'Defensa'!$B$6:$B$10,$A123,'Defensa'!$E$6:$E$10,"Ambos")</f>
         <v/>
       </c>
       <c r="E123" s="21">
-        <f>SUMIFS('S1'!$I$6:$I$32,'S1'!$B$6:$B$32,$A123,'S1'!$E$6:$E$32,"Diego")+SUMIFS('S1'!$I$6:$I$32,'S1'!$B$6:$B$32,$A123,'S1'!$E$6:$E$32,"Ambos")+SUMIFS('S2'!$I$6:$I$23,'S2'!$B$6:$B$23,$A123,'S2'!$E$6:$E$23,"Diego")+SUMIFS('S2'!$I$6:$I$23,'S2'!$B$6:$B$23,$A123,'S2'!$E$6:$E$23,"Ambos")+SUMIFS('S3'!$I$6:$I$19,'S3'!$B$6:$B$19,$A123,'S3'!$E$6:$E$19,"Diego")+SUMIFS('S3'!$I$6:$I$19,'S3'!$B$6:$B$19,$A123,'S3'!$E$6:$E$19,"Ambos")+SUMIFS('S4'!$I$6:$I$20,'S4'!$B$6:$B$20,$A123,'S4'!$E$6:$E$20,"Diego")+SUMIFS('S4'!$I$6:$I$20,'S4'!$B$6:$B$20,$A123,'S4'!$E$6:$E$20,"Ambos")+SUMIFS('S5'!$I$6:$I$20,'S5'!$B$6:$B$20,$A123,'S5'!$E$6:$E$20,"Diego")+SUMIFS('S5'!$I$6:$I$20,'S5'!$B$6:$B$20,$A123,'S5'!$E$6:$E$20,"Ambos")+SUMIFS('S6'!$I$6:$I$17,'S6'!$B$6:$B$17,$A123,'S6'!$E$6:$E$17,"Diego")+SUMIFS('S6'!$I$6:$I$17,'S6'!$B$6:$B$17,$A123,'S6'!$E$6:$E$17,"Ambos")+SUMIFS('S7'!$I$6:$I$19,'S7'!$B$6:$B$19,$A123,'S7'!$E$6:$E$19,"Diego")+SUMIFS('S7'!$I$6:$I$19,'S7'!$B$6:$B$19,$A123,'S7'!$E$6:$E$19,"Ambos")+SUMIFS('S8'!$I$6:$I$23,'S8'!$B$6:$B$23,$A123,'S8'!$E$6:$E$23,"Diego")+SUMIFS('S8'!$I$6:$I$23,'S8'!$B$6:$B$23,$A123,'S8'!$E$6:$E$23,"Ambos")+SUMIFS('S9'!$I$6:$I$15,'S9'!$B$6:$B$15,$A123,'S9'!$E$6:$E$15,"Diego")+SUMIFS('S9'!$I$6:$I$15,'S9'!$B$6:$B$15,$A123,'S9'!$E$6:$E$15,"Ambos")+SUMIFS('S10'!$I$6:$I$13,'S10'!$B$6:$B$13,$A123,'S10'!$E$6:$E$13,"Diego")+SUMIFS('S10'!$I$6:$I$13,'S10'!$B$6:$B$13,$A123,'S10'!$E$6:$E$13,"Ambos")+SUMIFS('Holgura'!$I$6:$I$11,'Holgura'!$B$6:$B$11,$A123,'Holgura'!$E$6:$E$11,"Diego")+SUMIFS('Holgura'!$I$6:$I$11,'Holgura'!$B$6:$B$11,$A123,'Holgura'!$E$6:$E$11,"Ambos")+SUMIFS('Entrega'!$I$6:$I$9,'Entrega'!$B$6:$B$9,$A123,'Entrega'!$E$6:$E$9,"Diego")+SUMIFS('Entrega'!$I$6:$I$9,'Entrega'!$B$6:$B$9,$A123,'Entrega'!$E$6:$E$9,"Ambos")+SUMIFS('Defensa'!$I$6:$I$10,'Defensa'!$B$6:$B$10,$A123,'Defensa'!$E$6:$E$10,"Diego")+SUMIFS('Defensa'!$I$6:$I$10,'Defensa'!$B$6:$B$10,$A123,'Defensa'!$E$6:$E$10,"Ambos")</f>
+        <f>SUMIFS('S1'!$I$6:$I$32,'S1'!$B$6:$B$32,$A123,'S1'!$E$6:$E$32,"Diego")+SUMIFS('S1'!$I$6:$I$32,'S1'!$B$6:$B$32,$A123,'S1'!$E$6:$E$32,"Ambos")+SUMIFS('S2'!$I$6:$I$23,'S2'!$B$6:$B$23,$A123,'S2'!$E$6:$E$23,"Diego")+SUMIFS('S2'!$I$6:$I$23,'S2'!$B$6:$B$23,$A123,'S2'!$E$6:$E$23,"Ambos")+SUMIFS('S3'!$I$6:$I$24,'S3'!$B$6:$B$24,$A123,'S3'!$E$6:$E$24,"Diego")+SUMIFS('S3'!$I$6:$I$24,'S3'!$B$6:$B$24,$A123,'S3'!$E$6:$E$24,"Ambos")+SUMIFS('S4'!$I$6:$I$22,'S4'!$B$6:$B$22,$A123,'S4'!$E$6:$E$22,"Diego")+SUMIFS('S4'!$I$6:$I$22,'S4'!$B$6:$B$22,$A123,'S4'!$E$6:$E$22,"Ambos")+SUMIFS('S5'!$I$6:$I$20,'S5'!$B$6:$B$20,$A123,'S5'!$E$6:$E$20,"Diego")+SUMIFS('S5'!$I$6:$I$20,'S5'!$B$6:$B$20,$A123,'S5'!$E$6:$E$20,"Ambos")+SUMIFS('S6'!$I$6:$I$17,'S6'!$B$6:$B$17,$A123,'S6'!$E$6:$E$17,"Diego")+SUMIFS('S6'!$I$6:$I$17,'S6'!$B$6:$B$17,$A123,'S6'!$E$6:$E$17,"Ambos")+SUMIFS('S7'!$I$6:$I$19,'S7'!$B$6:$B$19,$A123,'S7'!$E$6:$E$19,"Diego")+SUMIFS('S7'!$I$6:$I$19,'S7'!$B$6:$B$19,$A123,'S7'!$E$6:$E$19,"Ambos")+SUMIFS('S8'!$I$6:$I$23,'S8'!$B$6:$B$23,$A123,'S8'!$E$6:$E$23,"Diego")+SUMIFS('S8'!$I$6:$I$23,'S8'!$B$6:$B$23,$A123,'S8'!$E$6:$E$23,"Ambos")+SUMIFS('S9'!$I$6:$I$15,'S9'!$B$6:$B$15,$A123,'S9'!$E$6:$E$15,"Diego")+SUMIFS('S9'!$I$6:$I$15,'S9'!$B$6:$B$15,$A123,'S9'!$E$6:$E$15,"Ambos")+SUMIFS('S10'!$I$6:$I$13,'S10'!$B$6:$B$13,$A123,'S10'!$E$6:$E$13,"Diego")+SUMIFS('S10'!$I$6:$I$13,'S10'!$B$6:$B$13,$A123,'S10'!$E$6:$E$13,"Ambos")+SUMIFS('Holgura'!$I$6:$I$11,'Holgura'!$B$6:$B$11,$A123,'Holgura'!$E$6:$E$11,"Diego")+SUMIFS('Holgura'!$I$6:$I$11,'Holgura'!$B$6:$B$11,$A123,'Holgura'!$E$6:$E$11,"Ambos")+SUMIFS('Entrega'!$I$6:$I$9,'Entrega'!$B$6:$B$9,$A123,'Entrega'!$E$6:$E$9,"Diego")+SUMIFS('Entrega'!$I$6:$I$9,'Entrega'!$B$6:$B$9,$A123,'Entrega'!$E$6:$E$9,"Ambos")+SUMIFS('Defensa'!$I$6:$I$10,'Defensa'!$B$6:$B$10,$A123,'Defensa'!$E$6:$E$10,"Diego")+SUMIFS('Defensa'!$I$6:$I$10,'Defensa'!$B$6:$B$10,$A123,'Defensa'!$E$6:$E$10,"Ambos")</f>
         <v/>
       </c>
       <c r="F123" s="21">
-        <f>COUNTIFS('S1'!$B$6:$B$32,$A123,'S1'!$E$6:$E$32,"Víctor")+COUNTIFS('S1'!$B$6:$B$32,$A123,'S1'!$E$6:$E$32,"Ambos")+COUNTIFS('S2'!$B$6:$B$23,$A123,'S2'!$E$6:$E$23,"Víctor")+COUNTIFS('S2'!$B$6:$B$23,$A123,'S2'!$E$6:$E$23,"Ambos")+COUNTIFS('S3'!$B$6:$B$19,$A123,'S3'!$E$6:$E$19,"Víctor")+COUNTIFS('S3'!$B$6:$B$19,$A123,'S3'!$E$6:$E$19,"Ambos")+COUNTIFS('S4'!$B$6:$B$20,$A123,'S4'!$E$6:$E$20,"Víctor")+COUNTIFS('S4'!$B$6:$B$20,$A123,'S4'!$E$6:$E$20,"Ambos")+COUNTIFS('S5'!$B$6:$B$20,$A123,'S5'!$E$6:$E$20,"Víctor")+COUNTIFS('S5'!$B$6:$B$20,$A123,'S5'!$E$6:$E$20,"Ambos")+COUNTIFS('S6'!$B$6:$B$17,$A123,'S6'!$E$6:$E$17,"Víctor")+COUNTIFS('S6'!$B$6:$B$17,$A123,'S6'!$E$6:$E$17,"Ambos")+COUNTIFS('S7'!$B$6:$B$19,$A123,'S7'!$E$6:$E$19,"Víctor")+COUNTIFS('S7'!$B$6:$B$19,$A123,'S7'!$E$6:$E$19,"Ambos")+COUNTIFS('S8'!$B$6:$B$23,$A123,'S8'!$E$6:$E$23,"Víctor")+COUNTIFS('S8'!$B$6:$B$23,$A123,'S8'!$E$6:$E$23,"Ambos")+COUNTIFS('S9'!$B$6:$B$15,$A123,'S9'!$E$6:$E$15,"Víctor")+COUNTIFS('S9'!$B$6:$B$15,$A123,'S9'!$E$6:$E$15,"Ambos")+COUNTIFS('S10'!$B$6:$B$13,$A123,'S10'!$E$6:$E$13,"Víctor")+COUNTIFS('S10'!$B$6:$B$13,$A123,'S10'!$E$6:$E$13,"Ambos")+COUNTIFS('Holgura'!$B$6:$B$11,$A123,'Holgura'!$E$6:$E$11,"Víctor")+COUNTIFS('Holgura'!$B$6:$B$11,$A123,'Holgura'!$E$6:$E$11,"Ambos")+COUNTIFS('Entrega'!$B$6:$B$9,$A123,'Entrega'!$E$6:$E$9,"Víctor")+COUNTIFS('Entrega'!$B$6:$B$9,$A123,'Entrega'!$E$6:$E$9,"Ambos")+COUNTIFS('Defensa'!$B$6:$B$10,$A123,'Defensa'!$E$6:$E$10,"Víctor")+COUNTIFS('Defensa'!$B$6:$B$10,$A123,'Defensa'!$E$6:$E$10,"Ambos")</f>
+        <f>COUNTIFS('S1'!$B$6:$B$32,$A123,'S1'!$E$6:$E$32,"Víctor")+COUNTIFS('S1'!$B$6:$B$32,$A123,'S1'!$E$6:$E$32,"Ambos")+COUNTIFS('S2'!$B$6:$B$23,$A123,'S2'!$E$6:$E$23,"Víctor")+COUNTIFS('S2'!$B$6:$B$23,$A123,'S2'!$E$6:$E$23,"Ambos")+COUNTIFS('S3'!$B$6:$B$24,$A123,'S3'!$E$6:$E$24,"Víctor")+COUNTIFS('S3'!$B$6:$B$24,$A123,'S3'!$E$6:$E$24,"Ambos")+COUNTIFS('S4'!$B$6:$B$22,$A123,'S4'!$E$6:$E$22,"Víctor")+COUNTIFS('S4'!$B$6:$B$22,$A123,'S4'!$E$6:$E$22,"Ambos")+COUNTIFS('S5'!$B$6:$B$20,$A123,'S5'!$E$6:$E$20,"Víctor")+COUNTIFS('S5'!$B$6:$B$20,$A123,'S5'!$E$6:$E$20,"Ambos")+COUNTIFS('S6'!$B$6:$B$17,$A123,'S6'!$E$6:$E$17,"Víctor")+COUNTIFS('S6'!$B$6:$B$17,$A123,'S6'!$E$6:$E$17,"Ambos")+COUNTIFS('S7'!$B$6:$B$19,$A123,'S7'!$E$6:$E$19,"Víctor")+COUNTIFS('S7'!$B$6:$B$19,$A123,'S7'!$E$6:$E$19,"Ambos")+COUNTIFS('S8'!$B$6:$B$23,$A123,'S8'!$E$6:$E$23,"Víctor")+COUNTIFS('S8'!$B$6:$B$23,$A123,'S8'!$E$6:$E$23,"Ambos")+COUNTIFS('S9'!$B$6:$B$15,$A123,'S9'!$E$6:$E$15,"Víctor")+COUNTIFS('S9'!$B$6:$B$15,$A123,'S9'!$E$6:$E$15,"Ambos")+COUNTIFS('S10'!$B$6:$B$13,$A123,'S10'!$E$6:$E$13,"Víctor")+COUNTIFS('S10'!$B$6:$B$13,$A123,'S10'!$E$6:$E$13,"Ambos")+COUNTIFS('Holgura'!$B$6:$B$11,$A123,'Holgura'!$E$6:$E$11,"Víctor")+COUNTIFS('Holgura'!$B$6:$B$11,$A123,'Holgura'!$E$6:$E$11,"Ambos")+COUNTIFS('Entrega'!$B$6:$B$9,$A123,'Entrega'!$E$6:$E$9,"Víctor")+COUNTIFS('Entrega'!$B$6:$B$9,$A123,'Entrega'!$E$6:$E$9,"Ambos")+COUNTIFS('Defensa'!$B$6:$B$10,$A123,'Defensa'!$E$6:$E$10,"Víctor")+COUNTIFS('Defensa'!$B$6:$B$10,$A123,'Defensa'!$E$6:$E$10,"Ambos")</f>
         <v/>
       </c>
       <c r="G123" s="21">
-        <f>COUNTIFS('S1'!$B$6:$B$32,$A123,'S1'!$E$6:$E$32,"Diego")+COUNTIFS('S1'!$B$6:$B$32,$A123,'S1'!$E$6:$E$32,"Ambos")+COUNTIFS('S2'!$B$6:$B$23,$A123,'S2'!$E$6:$E$23,"Diego")+COUNTIFS('S2'!$B$6:$B$23,$A123,'S2'!$E$6:$E$23,"Ambos")+COUNTIFS('S3'!$B$6:$B$19,$A123,'S3'!$E$6:$E$19,"Diego")+COUNTIFS('S3'!$B$6:$B$19,$A123,'S3'!$E$6:$E$19,"Ambos")+COUNTIFS('S4'!$B$6:$B$20,$A123,'S4'!$E$6:$E$20,"Diego")+COUNTIFS('S4'!$B$6:$B$20,$A123,'S4'!$E$6:$E$20,"Ambos")+COUNTIFS('S5'!$B$6:$B$20,$A123,'S5'!$E$6:$E$20,"Diego")+COUNTIFS('S5'!$B$6:$B$20,$A123,'S5'!$E$6:$E$20,"Ambos")+COUNTIFS('S6'!$B$6:$B$17,$A123,'S6'!$E$6:$E$17,"Diego")+COUNTIFS('S6'!$B$6:$B$17,$A123,'S6'!$E$6:$E$17,"Ambos")+COUNTIFS('S7'!$B$6:$B$19,$A123,'S7'!$E$6:$E$19,"Diego")+COUNTIFS('S7'!$B$6:$B$19,$A123,'S7'!$E$6:$E$19,"Ambos")+COUNTIFS('S8'!$B$6:$B$23,$A123,'S8'!$E$6:$E$23,"Diego")+COUNTIFS('S8'!$B$6:$B$23,$A123,'S8'!$E$6:$E$23,"Ambos")+COUNTIFS('S9'!$B$6:$B$15,$A123,'S9'!$E$6:$E$15,"Diego")+COUNTIFS('S9'!$B$6:$B$15,$A123,'S9'!$E$6:$E$15,"Ambos")+COUNTIFS('S10'!$B$6:$B$13,$A123,'S10'!$E$6:$E$13,"Diego")+COUNTIFS('S10'!$B$6:$B$13,$A123,'S10'!$E$6:$E$13,"Ambos")+COUNTIFS('Holgura'!$B$6:$B$11,$A123,'Holgura'!$E$6:$E$11,"Diego")+COUNTIFS('Holgura'!$B$6:$B$11,$A123,'Holgura'!$E$6:$E$11,"Ambos")+COUNTIFS('Entrega'!$B$6:$B$9,$A123,'Entrega'!$E$6:$E$9,"Diego")+COUNTIFS('Entrega'!$B$6:$B$9,$A123,'Entrega'!$E$6:$E$9,"Ambos")+COUNTIFS('Defensa'!$B$6:$B$10,$A123,'Defensa'!$E$6:$E$10,"Diego")+COUNTIFS('Defensa'!$B$6:$B$10,$A123,'Defensa'!$E$6:$E$10,"Ambos")</f>
+        <f>COUNTIFS('S1'!$B$6:$B$32,$A123,'S1'!$E$6:$E$32,"Diego")+COUNTIFS('S1'!$B$6:$B$32,$A123,'S1'!$E$6:$E$32,"Ambos")+COUNTIFS('S2'!$B$6:$B$23,$A123,'S2'!$E$6:$E$23,"Diego")+COUNTIFS('S2'!$B$6:$B$23,$A123,'S2'!$E$6:$E$23,"Ambos")+COUNTIFS('S3'!$B$6:$B$24,$A123,'S3'!$E$6:$E$24,"Diego")+COUNTIFS('S3'!$B$6:$B$24,$A123,'S3'!$E$6:$E$24,"Ambos")+COUNTIFS('S4'!$B$6:$B$22,$A123,'S4'!$E$6:$E$22,"Diego")+COUNTIFS('S4'!$B$6:$B$22,$A123,'S4'!$E$6:$E$22,"Ambos")+COUNTIFS('S5'!$B$6:$B$20,$A123,'S5'!$E$6:$E$20,"Diego")+COUNTIFS('S5'!$B$6:$B$20,$A123,'S5'!$E$6:$E$20,"Ambos")+COUNTIFS('S6'!$B$6:$B$17,$A123,'S6'!$E$6:$E$17,"Diego")+COUNTIFS('S6'!$B$6:$B$17,$A123,'S6'!$E$6:$E$17,"Ambos")+COUNTIFS('S7'!$B$6:$B$19,$A123,'S7'!$E$6:$E$19,"Diego")+COUNTIFS('S7'!$B$6:$B$19,$A123,'S7'!$E$6:$E$19,"Ambos")+COUNTIFS('S8'!$B$6:$B$23,$A123,'S8'!$E$6:$E$23,"Diego")+COUNTIFS('S8'!$B$6:$B$23,$A123,'S8'!$E$6:$E$23,"Ambos")+COUNTIFS('S9'!$B$6:$B$15,$A123,'S9'!$E$6:$E$15,"Diego")+COUNTIFS('S9'!$B$6:$B$15,$A123,'S9'!$E$6:$E$15,"Ambos")+COUNTIFS('S10'!$B$6:$B$13,$A123,'S10'!$E$6:$E$13,"Diego")+COUNTIFS('S10'!$B$6:$B$13,$A123,'S10'!$E$6:$E$13,"Ambos")+COUNTIFS('Holgura'!$B$6:$B$11,$A123,'Holgura'!$E$6:$E$11,"Diego")+COUNTIFS('Holgura'!$B$6:$B$11,$A123,'Holgura'!$E$6:$E$11,"Ambos")+COUNTIFS('Entrega'!$B$6:$B$9,$A123,'Entrega'!$E$6:$E$9,"Diego")+COUNTIFS('Entrega'!$B$6:$B$9,$A123,'Entrega'!$E$6:$E$9,"Ambos")+COUNTIFS('Defensa'!$B$6:$B$10,$A123,'Defensa'!$E$6:$E$10,"Diego")+COUNTIFS('Defensa'!$B$6:$B$10,$A123,'Defensa'!$E$6:$E$10,"Ambos")</f>
         <v/>
       </c>
     </row>
@@ -12131,19 +12152,19 @@
         <v/>
       </c>
       <c r="D124" s="21">
-        <f>SUMIFS('S1'!$I$6:$I$32,'S1'!$B$6:$B$32,$A124,'S1'!$E$6:$E$32,"Víctor")+SUMIFS('S1'!$I$6:$I$32,'S1'!$B$6:$B$32,$A124,'S1'!$E$6:$E$32,"Ambos")+SUMIFS('S2'!$I$6:$I$23,'S2'!$B$6:$B$23,$A124,'S2'!$E$6:$E$23,"Víctor")+SUMIFS('S2'!$I$6:$I$23,'S2'!$B$6:$B$23,$A124,'S2'!$E$6:$E$23,"Ambos")+SUMIFS('S3'!$I$6:$I$19,'S3'!$B$6:$B$19,$A124,'S3'!$E$6:$E$19,"Víctor")+SUMIFS('S3'!$I$6:$I$19,'S3'!$B$6:$B$19,$A124,'S3'!$E$6:$E$19,"Ambos")+SUMIFS('S4'!$I$6:$I$20,'S4'!$B$6:$B$20,$A124,'S4'!$E$6:$E$20,"Víctor")+SUMIFS('S4'!$I$6:$I$20,'S4'!$B$6:$B$20,$A124,'S4'!$E$6:$E$20,"Ambos")+SUMIFS('S5'!$I$6:$I$20,'S5'!$B$6:$B$20,$A124,'S5'!$E$6:$E$20,"Víctor")+SUMIFS('S5'!$I$6:$I$20,'S5'!$B$6:$B$20,$A124,'S5'!$E$6:$E$20,"Ambos")+SUMIFS('S6'!$I$6:$I$17,'S6'!$B$6:$B$17,$A124,'S6'!$E$6:$E$17,"Víctor")+SUMIFS('S6'!$I$6:$I$17,'S6'!$B$6:$B$17,$A124,'S6'!$E$6:$E$17,"Ambos")+SUMIFS('S7'!$I$6:$I$19,'S7'!$B$6:$B$19,$A124,'S7'!$E$6:$E$19,"Víctor")+SUMIFS('S7'!$I$6:$I$19,'S7'!$B$6:$B$19,$A124,'S7'!$E$6:$E$19,"Ambos")+SUMIFS('S8'!$I$6:$I$23,'S8'!$B$6:$B$23,$A124,'S8'!$E$6:$E$23,"Víctor")+SUMIFS('S8'!$I$6:$I$23,'S8'!$B$6:$B$23,$A124,'S8'!$E$6:$E$23,"Ambos")+SUMIFS('S9'!$I$6:$I$15,'S9'!$B$6:$B$15,$A124,'S9'!$E$6:$E$15,"Víctor")+SUMIFS('S9'!$I$6:$I$15,'S9'!$B$6:$B$15,$A124,'S9'!$E$6:$E$15,"Ambos")+SUMIFS('S10'!$I$6:$I$13,'S10'!$B$6:$B$13,$A124,'S10'!$E$6:$E$13,"Víctor")+SUMIFS('S10'!$I$6:$I$13,'S10'!$B$6:$B$13,$A124,'S10'!$E$6:$E$13,"Ambos")+SUMIFS('Holgura'!$I$6:$I$11,'Holgura'!$B$6:$B$11,$A124,'Holgura'!$E$6:$E$11,"Víctor")+SUMIFS('Holgura'!$I$6:$I$11,'Holgura'!$B$6:$B$11,$A124,'Holgura'!$E$6:$E$11,"Ambos")+SUMIFS('Entrega'!$I$6:$I$9,'Entrega'!$B$6:$B$9,$A124,'Entrega'!$E$6:$E$9,"Víctor")+SUMIFS('Entrega'!$I$6:$I$9,'Entrega'!$B$6:$B$9,$A124,'Entrega'!$E$6:$E$9,"Ambos")+SUMIFS('Defensa'!$I$6:$I$10,'Defensa'!$B$6:$B$10,$A124,'Defensa'!$E$6:$E$10,"Víctor")+SUMIFS('Defensa'!$I$6:$I$10,'Defensa'!$B$6:$B$10,$A124,'Defensa'!$E$6:$E$10,"Ambos")</f>
+        <f>SUMIFS('S1'!$I$6:$I$32,'S1'!$B$6:$B$32,$A124,'S1'!$E$6:$E$32,"Víctor")+SUMIFS('S1'!$I$6:$I$32,'S1'!$B$6:$B$32,$A124,'S1'!$E$6:$E$32,"Ambos")+SUMIFS('S2'!$I$6:$I$23,'S2'!$B$6:$B$23,$A124,'S2'!$E$6:$E$23,"Víctor")+SUMIFS('S2'!$I$6:$I$23,'S2'!$B$6:$B$23,$A124,'S2'!$E$6:$E$23,"Ambos")+SUMIFS('S3'!$I$6:$I$24,'S3'!$B$6:$B$24,$A124,'S3'!$E$6:$E$24,"Víctor")+SUMIFS('S3'!$I$6:$I$24,'S3'!$B$6:$B$24,$A124,'S3'!$E$6:$E$24,"Ambos")+SUMIFS('S4'!$I$6:$I$22,'S4'!$B$6:$B$22,$A124,'S4'!$E$6:$E$22,"Víctor")+SUMIFS('S4'!$I$6:$I$22,'S4'!$B$6:$B$22,$A124,'S4'!$E$6:$E$22,"Ambos")+SUMIFS('S5'!$I$6:$I$20,'S5'!$B$6:$B$20,$A124,'S5'!$E$6:$E$20,"Víctor")+SUMIFS('S5'!$I$6:$I$20,'S5'!$B$6:$B$20,$A124,'S5'!$E$6:$E$20,"Ambos")+SUMIFS('S6'!$I$6:$I$17,'S6'!$B$6:$B$17,$A124,'S6'!$E$6:$E$17,"Víctor")+SUMIFS('S6'!$I$6:$I$17,'S6'!$B$6:$B$17,$A124,'S6'!$E$6:$E$17,"Ambos")+SUMIFS('S7'!$I$6:$I$19,'S7'!$B$6:$B$19,$A124,'S7'!$E$6:$E$19,"Víctor")+SUMIFS('S7'!$I$6:$I$19,'S7'!$B$6:$B$19,$A124,'S7'!$E$6:$E$19,"Ambos")+SUMIFS('S8'!$I$6:$I$23,'S8'!$B$6:$B$23,$A124,'S8'!$E$6:$E$23,"Víctor")+SUMIFS('S8'!$I$6:$I$23,'S8'!$B$6:$B$23,$A124,'S8'!$E$6:$E$23,"Ambos")+SUMIFS('S9'!$I$6:$I$15,'S9'!$B$6:$B$15,$A124,'S9'!$E$6:$E$15,"Víctor")+SUMIFS('S9'!$I$6:$I$15,'S9'!$B$6:$B$15,$A124,'S9'!$E$6:$E$15,"Ambos")+SUMIFS('S10'!$I$6:$I$13,'S10'!$B$6:$B$13,$A124,'S10'!$E$6:$E$13,"Víctor")+SUMIFS('S10'!$I$6:$I$13,'S10'!$B$6:$B$13,$A124,'S10'!$E$6:$E$13,"Ambos")+SUMIFS('Holgura'!$I$6:$I$11,'Holgura'!$B$6:$B$11,$A124,'Holgura'!$E$6:$E$11,"Víctor")+SUMIFS('Holgura'!$I$6:$I$11,'Holgura'!$B$6:$B$11,$A124,'Holgura'!$E$6:$E$11,"Ambos")+SUMIFS('Entrega'!$I$6:$I$9,'Entrega'!$B$6:$B$9,$A124,'Entrega'!$E$6:$E$9,"Víctor")+SUMIFS('Entrega'!$I$6:$I$9,'Entrega'!$B$6:$B$9,$A124,'Entrega'!$E$6:$E$9,"Ambos")+SUMIFS('Defensa'!$I$6:$I$10,'Defensa'!$B$6:$B$10,$A124,'Defensa'!$E$6:$E$10,"Víctor")+SUMIFS('Defensa'!$I$6:$I$10,'Defensa'!$B$6:$B$10,$A124,'Defensa'!$E$6:$E$10,"Ambos")</f>
         <v/>
       </c>
       <c r="E124" s="21">
-        <f>SUMIFS('S1'!$I$6:$I$32,'S1'!$B$6:$B$32,$A124,'S1'!$E$6:$E$32,"Diego")+SUMIFS('S1'!$I$6:$I$32,'S1'!$B$6:$B$32,$A124,'S1'!$E$6:$E$32,"Ambos")+SUMIFS('S2'!$I$6:$I$23,'S2'!$B$6:$B$23,$A124,'S2'!$E$6:$E$23,"Diego")+SUMIFS('S2'!$I$6:$I$23,'S2'!$B$6:$B$23,$A124,'S2'!$E$6:$E$23,"Ambos")+SUMIFS('S3'!$I$6:$I$19,'S3'!$B$6:$B$19,$A124,'S3'!$E$6:$E$19,"Diego")+SUMIFS('S3'!$I$6:$I$19,'S3'!$B$6:$B$19,$A124,'S3'!$E$6:$E$19,"Ambos")+SUMIFS('S4'!$I$6:$I$20,'S4'!$B$6:$B$20,$A124,'S4'!$E$6:$E$20,"Diego")+SUMIFS('S4'!$I$6:$I$20,'S4'!$B$6:$B$20,$A124,'S4'!$E$6:$E$20,"Ambos")+SUMIFS('S5'!$I$6:$I$20,'S5'!$B$6:$B$20,$A124,'S5'!$E$6:$E$20,"Diego")+SUMIFS('S5'!$I$6:$I$20,'S5'!$B$6:$B$20,$A124,'S5'!$E$6:$E$20,"Ambos")+SUMIFS('S6'!$I$6:$I$17,'S6'!$B$6:$B$17,$A124,'S6'!$E$6:$E$17,"Diego")+SUMIFS('S6'!$I$6:$I$17,'S6'!$B$6:$B$17,$A124,'S6'!$E$6:$E$17,"Ambos")+SUMIFS('S7'!$I$6:$I$19,'S7'!$B$6:$B$19,$A124,'S7'!$E$6:$E$19,"Diego")+SUMIFS('S7'!$I$6:$I$19,'S7'!$B$6:$B$19,$A124,'S7'!$E$6:$E$19,"Ambos")+SUMIFS('S8'!$I$6:$I$23,'S8'!$B$6:$B$23,$A124,'S8'!$E$6:$E$23,"Diego")+SUMIFS('S8'!$I$6:$I$23,'S8'!$B$6:$B$23,$A124,'S8'!$E$6:$E$23,"Ambos")+SUMIFS('S9'!$I$6:$I$15,'S9'!$B$6:$B$15,$A124,'S9'!$E$6:$E$15,"Diego")+SUMIFS('S9'!$I$6:$I$15,'S9'!$B$6:$B$15,$A124,'S9'!$E$6:$E$15,"Ambos")+SUMIFS('S10'!$I$6:$I$13,'S10'!$B$6:$B$13,$A124,'S10'!$E$6:$E$13,"Diego")+SUMIFS('S10'!$I$6:$I$13,'S10'!$B$6:$B$13,$A124,'S10'!$E$6:$E$13,"Ambos")+SUMIFS('Holgura'!$I$6:$I$11,'Holgura'!$B$6:$B$11,$A124,'Holgura'!$E$6:$E$11,"Diego")+SUMIFS('Holgura'!$I$6:$I$11,'Holgura'!$B$6:$B$11,$A124,'Holgura'!$E$6:$E$11,"Ambos")+SUMIFS('Entrega'!$I$6:$I$9,'Entrega'!$B$6:$B$9,$A124,'Entrega'!$E$6:$E$9,"Diego")+SUMIFS('Entrega'!$I$6:$I$9,'Entrega'!$B$6:$B$9,$A124,'Entrega'!$E$6:$E$9,"Ambos")+SUMIFS('Defensa'!$I$6:$I$10,'Defensa'!$B$6:$B$10,$A124,'Defensa'!$E$6:$E$10,"Diego")+SUMIFS('Defensa'!$I$6:$I$10,'Defensa'!$B$6:$B$10,$A124,'Defensa'!$E$6:$E$10,"Ambos")</f>
+        <f>SUMIFS('S1'!$I$6:$I$32,'S1'!$B$6:$B$32,$A124,'S1'!$E$6:$E$32,"Diego")+SUMIFS('S1'!$I$6:$I$32,'S1'!$B$6:$B$32,$A124,'S1'!$E$6:$E$32,"Ambos")+SUMIFS('S2'!$I$6:$I$23,'S2'!$B$6:$B$23,$A124,'S2'!$E$6:$E$23,"Diego")+SUMIFS('S2'!$I$6:$I$23,'S2'!$B$6:$B$23,$A124,'S2'!$E$6:$E$23,"Ambos")+SUMIFS('S3'!$I$6:$I$24,'S3'!$B$6:$B$24,$A124,'S3'!$E$6:$E$24,"Diego")+SUMIFS('S3'!$I$6:$I$24,'S3'!$B$6:$B$24,$A124,'S3'!$E$6:$E$24,"Ambos")+SUMIFS('S4'!$I$6:$I$22,'S4'!$B$6:$B$22,$A124,'S4'!$E$6:$E$22,"Diego")+SUMIFS('S4'!$I$6:$I$22,'S4'!$B$6:$B$22,$A124,'S4'!$E$6:$E$22,"Ambos")+SUMIFS('S5'!$I$6:$I$20,'S5'!$B$6:$B$20,$A124,'S5'!$E$6:$E$20,"Diego")+SUMIFS('S5'!$I$6:$I$20,'S5'!$B$6:$B$20,$A124,'S5'!$E$6:$E$20,"Ambos")+SUMIFS('S6'!$I$6:$I$17,'S6'!$B$6:$B$17,$A124,'S6'!$E$6:$E$17,"Diego")+SUMIFS('S6'!$I$6:$I$17,'S6'!$B$6:$B$17,$A124,'S6'!$E$6:$E$17,"Ambos")+SUMIFS('S7'!$I$6:$I$19,'S7'!$B$6:$B$19,$A124,'S7'!$E$6:$E$19,"Diego")+SUMIFS('S7'!$I$6:$I$19,'S7'!$B$6:$B$19,$A124,'S7'!$E$6:$E$19,"Ambos")+SUMIFS('S8'!$I$6:$I$23,'S8'!$B$6:$B$23,$A124,'S8'!$E$6:$E$23,"Diego")+SUMIFS('S8'!$I$6:$I$23,'S8'!$B$6:$B$23,$A124,'S8'!$E$6:$E$23,"Ambos")+SUMIFS('S9'!$I$6:$I$15,'S9'!$B$6:$B$15,$A124,'S9'!$E$6:$E$15,"Diego")+SUMIFS('S9'!$I$6:$I$15,'S9'!$B$6:$B$15,$A124,'S9'!$E$6:$E$15,"Ambos")+SUMIFS('S10'!$I$6:$I$13,'S10'!$B$6:$B$13,$A124,'S10'!$E$6:$E$13,"Diego")+SUMIFS('S10'!$I$6:$I$13,'S10'!$B$6:$B$13,$A124,'S10'!$E$6:$E$13,"Ambos")+SUMIFS('Holgura'!$I$6:$I$11,'Holgura'!$B$6:$B$11,$A124,'Holgura'!$E$6:$E$11,"Diego")+SUMIFS('Holgura'!$I$6:$I$11,'Holgura'!$B$6:$B$11,$A124,'Holgura'!$E$6:$E$11,"Ambos")+SUMIFS('Entrega'!$I$6:$I$9,'Entrega'!$B$6:$B$9,$A124,'Entrega'!$E$6:$E$9,"Diego")+SUMIFS('Entrega'!$I$6:$I$9,'Entrega'!$B$6:$B$9,$A124,'Entrega'!$E$6:$E$9,"Ambos")+SUMIFS('Defensa'!$I$6:$I$10,'Defensa'!$B$6:$B$10,$A124,'Defensa'!$E$6:$E$10,"Diego")+SUMIFS('Defensa'!$I$6:$I$10,'Defensa'!$B$6:$B$10,$A124,'Defensa'!$E$6:$E$10,"Ambos")</f>
         <v/>
       </c>
       <c r="F124" s="21">
-        <f>COUNTIFS('S1'!$B$6:$B$32,$A124,'S1'!$E$6:$E$32,"Víctor")+COUNTIFS('S1'!$B$6:$B$32,$A124,'S1'!$E$6:$E$32,"Ambos")+COUNTIFS('S2'!$B$6:$B$23,$A124,'S2'!$E$6:$E$23,"Víctor")+COUNTIFS('S2'!$B$6:$B$23,$A124,'S2'!$E$6:$E$23,"Ambos")+COUNTIFS('S3'!$B$6:$B$19,$A124,'S3'!$E$6:$E$19,"Víctor")+COUNTIFS('S3'!$B$6:$B$19,$A124,'S3'!$E$6:$E$19,"Ambos")+COUNTIFS('S4'!$B$6:$B$20,$A124,'S4'!$E$6:$E$20,"Víctor")+COUNTIFS('S4'!$B$6:$B$20,$A124,'S4'!$E$6:$E$20,"Ambos")+COUNTIFS('S5'!$B$6:$B$20,$A124,'S5'!$E$6:$E$20,"Víctor")+COUNTIFS('S5'!$B$6:$B$20,$A124,'S5'!$E$6:$E$20,"Ambos")+COUNTIFS('S6'!$B$6:$B$17,$A124,'S6'!$E$6:$E$17,"Víctor")+COUNTIFS('S6'!$B$6:$B$17,$A124,'S6'!$E$6:$E$17,"Ambos")+COUNTIFS('S7'!$B$6:$B$19,$A124,'S7'!$E$6:$E$19,"Víctor")+COUNTIFS('S7'!$B$6:$B$19,$A124,'S7'!$E$6:$E$19,"Ambos")+COUNTIFS('S8'!$B$6:$B$23,$A124,'S8'!$E$6:$E$23,"Víctor")+COUNTIFS('S8'!$B$6:$B$23,$A124,'S8'!$E$6:$E$23,"Ambos")+COUNTIFS('S9'!$B$6:$B$15,$A124,'S9'!$E$6:$E$15,"Víctor")+COUNTIFS('S9'!$B$6:$B$15,$A124,'S9'!$E$6:$E$15,"Ambos")+COUNTIFS('S10'!$B$6:$B$13,$A124,'S10'!$E$6:$E$13,"Víctor")+COUNTIFS('S10'!$B$6:$B$13,$A124,'S10'!$E$6:$E$13,"Ambos")+COUNTIFS('Holgura'!$B$6:$B$11,$A124,'Holgura'!$E$6:$E$11,"Víctor")+COUNTIFS('Holgura'!$B$6:$B$11,$A124,'Holgura'!$E$6:$E$11,"Ambos")+COUNTIFS('Entrega'!$B$6:$B$9,$A124,'Entrega'!$E$6:$E$9,"Víctor")+COUNTIFS('Entrega'!$B$6:$B$9,$A124,'Entrega'!$E$6:$E$9,"Ambos")+COUNTIFS('Defensa'!$B$6:$B$10,$A124,'Defensa'!$E$6:$E$10,"Víctor")+COUNTIFS('Defensa'!$B$6:$B$10,$A124,'Defensa'!$E$6:$E$10,"Ambos")</f>
+        <f>COUNTIFS('S1'!$B$6:$B$32,$A124,'S1'!$E$6:$E$32,"Víctor")+COUNTIFS('S1'!$B$6:$B$32,$A124,'S1'!$E$6:$E$32,"Ambos")+COUNTIFS('S2'!$B$6:$B$23,$A124,'S2'!$E$6:$E$23,"Víctor")+COUNTIFS('S2'!$B$6:$B$23,$A124,'S2'!$E$6:$E$23,"Ambos")+COUNTIFS('S3'!$B$6:$B$24,$A124,'S3'!$E$6:$E$24,"Víctor")+COUNTIFS('S3'!$B$6:$B$24,$A124,'S3'!$E$6:$E$24,"Ambos")+COUNTIFS('S4'!$B$6:$B$22,$A124,'S4'!$E$6:$E$22,"Víctor")+COUNTIFS('S4'!$B$6:$B$22,$A124,'S4'!$E$6:$E$22,"Ambos")+COUNTIFS('S5'!$B$6:$B$20,$A124,'S5'!$E$6:$E$20,"Víctor")+COUNTIFS('S5'!$B$6:$B$20,$A124,'S5'!$E$6:$E$20,"Ambos")+COUNTIFS('S6'!$B$6:$B$17,$A124,'S6'!$E$6:$E$17,"Víctor")+COUNTIFS('S6'!$B$6:$B$17,$A124,'S6'!$E$6:$E$17,"Ambos")+COUNTIFS('S7'!$B$6:$B$19,$A124,'S7'!$E$6:$E$19,"Víctor")+COUNTIFS('S7'!$B$6:$B$19,$A124,'S7'!$E$6:$E$19,"Ambos")+COUNTIFS('S8'!$B$6:$B$23,$A124,'S8'!$E$6:$E$23,"Víctor")+COUNTIFS('S8'!$B$6:$B$23,$A124,'S8'!$E$6:$E$23,"Ambos")+COUNTIFS('S9'!$B$6:$B$15,$A124,'S9'!$E$6:$E$15,"Víctor")+COUNTIFS('S9'!$B$6:$B$15,$A124,'S9'!$E$6:$E$15,"Ambos")+COUNTIFS('S10'!$B$6:$B$13,$A124,'S10'!$E$6:$E$13,"Víctor")+COUNTIFS('S10'!$B$6:$B$13,$A124,'S10'!$E$6:$E$13,"Ambos")+COUNTIFS('Holgura'!$B$6:$B$11,$A124,'Holgura'!$E$6:$E$11,"Víctor")+COUNTIFS('Holgura'!$B$6:$B$11,$A124,'Holgura'!$E$6:$E$11,"Ambos")+COUNTIFS('Entrega'!$B$6:$B$9,$A124,'Entrega'!$E$6:$E$9,"Víctor")+COUNTIFS('Entrega'!$B$6:$B$9,$A124,'Entrega'!$E$6:$E$9,"Ambos")+COUNTIFS('Defensa'!$B$6:$B$10,$A124,'Defensa'!$E$6:$E$10,"Víctor")+COUNTIFS('Defensa'!$B$6:$B$10,$A124,'Defensa'!$E$6:$E$10,"Ambos")</f>
         <v/>
       </c>
       <c r="G124" s="21">
-        <f>COUNTIFS('S1'!$B$6:$B$32,$A124,'S1'!$E$6:$E$32,"Diego")+COUNTIFS('S1'!$B$6:$B$32,$A124,'S1'!$E$6:$E$32,"Ambos")+COUNTIFS('S2'!$B$6:$B$23,$A124,'S2'!$E$6:$E$23,"Diego")+COUNTIFS('S2'!$B$6:$B$23,$A124,'S2'!$E$6:$E$23,"Ambos")+COUNTIFS('S3'!$B$6:$B$19,$A124,'S3'!$E$6:$E$19,"Diego")+COUNTIFS('S3'!$B$6:$B$19,$A124,'S3'!$E$6:$E$19,"Ambos")+COUNTIFS('S4'!$B$6:$B$20,$A124,'S4'!$E$6:$E$20,"Diego")+COUNTIFS('S4'!$B$6:$B$20,$A124,'S4'!$E$6:$E$20,"Ambos")+COUNTIFS('S5'!$B$6:$B$20,$A124,'S5'!$E$6:$E$20,"Diego")+COUNTIFS('S5'!$B$6:$B$20,$A124,'S5'!$E$6:$E$20,"Ambos")+COUNTIFS('S6'!$B$6:$B$17,$A124,'S6'!$E$6:$E$17,"Diego")+COUNTIFS('S6'!$B$6:$B$17,$A124,'S6'!$E$6:$E$17,"Ambos")+COUNTIFS('S7'!$B$6:$B$19,$A124,'S7'!$E$6:$E$19,"Diego")+COUNTIFS('S7'!$B$6:$B$19,$A124,'S7'!$E$6:$E$19,"Ambos")+COUNTIFS('S8'!$B$6:$B$23,$A124,'S8'!$E$6:$E$23,"Diego")+COUNTIFS('S8'!$B$6:$B$23,$A124,'S8'!$E$6:$E$23,"Ambos")+COUNTIFS('S9'!$B$6:$B$15,$A124,'S9'!$E$6:$E$15,"Diego")+COUNTIFS('S9'!$B$6:$B$15,$A124,'S9'!$E$6:$E$15,"Ambos")+COUNTIFS('S10'!$B$6:$B$13,$A124,'S10'!$E$6:$E$13,"Diego")+COUNTIFS('S10'!$B$6:$B$13,$A124,'S10'!$E$6:$E$13,"Ambos")+COUNTIFS('Holgura'!$B$6:$B$11,$A124,'Holgura'!$E$6:$E$11,"Diego")+COUNTIFS('Holgura'!$B$6:$B$11,$A124,'Holgura'!$E$6:$E$11,"Ambos")+COUNTIFS('Entrega'!$B$6:$B$9,$A124,'Entrega'!$E$6:$E$9,"Diego")+COUNTIFS('Entrega'!$B$6:$B$9,$A124,'Entrega'!$E$6:$E$9,"Ambos")+COUNTIFS('Defensa'!$B$6:$B$10,$A124,'Defensa'!$E$6:$E$10,"Diego")+COUNTIFS('Defensa'!$B$6:$B$10,$A124,'Defensa'!$E$6:$E$10,"Ambos")</f>
+        <f>COUNTIFS('S1'!$B$6:$B$32,$A124,'S1'!$E$6:$E$32,"Diego")+COUNTIFS('S1'!$B$6:$B$32,$A124,'S1'!$E$6:$E$32,"Ambos")+COUNTIFS('S2'!$B$6:$B$23,$A124,'S2'!$E$6:$E$23,"Diego")+COUNTIFS('S2'!$B$6:$B$23,$A124,'S2'!$E$6:$E$23,"Ambos")+COUNTIFS('S3'!$B$6:$B$24,$A124,'S3'!$E$6:$E$24,"Diego")+COUNTIFS('S3'!$B$6:$B$24,$A124,'S3'!$E$6:$E$24,"Ambos")+COUNTIFS('S4'!$B$6:$B$22,$A124,'S4'!$E$6:$E$22,"Diego")+COUNTIFS('S4'!$B$6:$B$22,$A124,'S4'!$E$6:$E$22,"Ambos")+COUNTIFS('S5'!$B$6:$B$20,$A124,'S5'!$E$6:$E$20,"Diego")+COUNTIFS('S5'!$B$6:$B$20,$A124,'S5'!$E$6:$E$20,"Ambos")+COUNTIFS('S6'!$B$6:$B$17,$A124,'S6'!$E$6:$E$17,"Diego")+COUNTIFS('S6'!$B$6:$B$17,$A124,'S6'!$E$6:$E$17,"Ambos")+COUNTIFS('S7'!$B$6:$B$19,$A124,'S7'!$E$6:$E$19,"Diego")+COUNTIFS('S7'!$B$6:$B$19,$A124,'S7'!$E$6:$E$19,"Ambos")+COUNTIFS('S8'!$B$6:$B$23,$A124,'S8'!$E$6:$E$23,"Diego")+COUNTIFS('S8'!$B$6:$B$23,$A124,'S8'!$E$6:$E$23,"Ambos")+COUNTIFS('S9'!$B$6:$B$15,$A124,'S9'!$E$6:$E$15,"Diego")+COUNTIFS('S9'!$B$6:$B$15,$A124,'S9'!$E$6:$E$15,"Ambos")+COUNTIFS('S10'!$B$6:$B$13,$A124,'S10'!$E$6:$E$13,"Diego")+COUNTIFS('S10'!$B$6:$B$13,$A124,'S10'!$E$6:$E$13,"Ambos")+COUNTIFS('Holgura'!$B$6:$B$11,$A124,'Holgura'!$E$6:$E$11,"Diego")+COUNTIFS('Holgura'!$B$6:$B$11,$A124,'Holgura'!$E$6:$E$11,"Ambos")+COUNTIFS('Entrega'!$B$6:$B$9,$A124,'Entrega'!$E$6:$E$9,"Diego")+COUNTIFS('Entrega'!$B$6:$B$9,$A124,'Entrega'!$E$6:$E$9,"Ambos")+COUNTIFS('Defensa'!$B$6:$B$10,$A124,'Defensa'!$E$6:$E$10,"Diego")+COUNTIFS('Defensa'!$B$6:$B$10,$A124,'Defensa'!$E$6:$E$10,"Ambos")</f>
         <v/>
       </c>
     </row>
@@ -12160,19 +12181,19 @@
         <v/>
       </c>
       <c r="D125" s="21">
-        <f>SUMIFS('S1'!$I$6:$I$32,'S1'!$B$6:$B$32,$A125,'S1'!$E$6:$E$32,"Víctor")+SUMIFS('S1'!$I$6:$I$32,'S1'!$B$6:$B$32,$A125,'S1'!$E$6:$E$32,"Ambos")+SUMIFS('S2'!$I$6:$I$23,'S2'!$B$6:$B$23,$A125,'S2'!$E$6:$E$23,"Víctor")+SUMIFS('S2'!$I$6:$I$23,'S2'!$B$6:$B$23,$A125,'S2'!$E$6:$E$23,"Ambos")+SUMIFS('S3'!$I$6:$I$19,'S3'!$B$6:$B$19,$A125,'S3'!$E$6:$E$19,"Víctor")+SUMIFS('S3'!$I$6:$I$19,'S3'!$B$6:$B$19,$A125,'S3'!$E$6:$E$19,"Ambos")+SUMIFS('S4'!$I$6:$I$20,'S4'!$B$6:$B$20,$A125,'S4'!$E$6:$E$20,"Víctor")+SUMIFS('S4'!$I$6:$I$20,'S4'!$B$6:$B$20,$A125,'S4'!$E$6:$E$20,"Ambos")+SUMIFS('S5'!$I$6:$I$20,'S5'!$B$6:$B$20,$A125,'S5'!$E$6:$E$20,"Víctor")+SUMIFS('S5'!$I$6:$I$20,'S5'!$B$6:$B$20,$A125,'S5'!$E$6:$E$20,"Ambos")+SUMIFS('S6'!$I$6:$I$17,'S6'!$B$6:$B$17,$A125,'S6'!$E$6:$E$17,"Víctor")+SUMIFS('S6'!$I$6:$I$17,'S6'!$B$6:$B$17,$A125,'S6'!$E$6:$E$17,"Ambos")+SUMIFS('S7'!$I$6:$I$19,'S7'!$B$6:$B$19,$A125,'S7'!$E$6:$E$19,"Víctor")+SUMIFS('S7'!$I$6:$I$19,'S7'!$B$6:$B$19,$A125,'S7'!$E$6:$E$19,"Ambos")+SUMIFS('S8'!$I$6:$I$23,'S8'!$B$6:$B$23,$A125,'S8'!$E$6:$E$23,"Víctor")+SUMIFS('S8'!$I$6:$I$23,'S8'!$B$6:$B$23,$A125,'S8'!$E$6:$E$23,"Ambos")+SUMIFS('S9'!$I$6:$I$15,'S9'!$B$6:$B$15,$A125,'S9'!$E$6:$E$15,"Víctor")+SUMIFS('S9'!$I$6:$I$15,'S9'!$B$6:$B$15,$A125,'S9'!$E$6:$E$15,"Ambos")+SUMIFS('S10'!$I$6:$I$13,'S10'!$B$6:$B$13,$A125,'S10'!$E$6:$E$13,"Víctor")+SUMIFS('S10'!$I$6:$I$13,'S10'!$B$6:$B$13,$A125,'S10'!$E$6:$E$13,"Ambos")+SUMIFS('Holgura'!$I$6:$I$11,'Holgura'!$B$6:$B$11,$A125,'Holgura'!$E$6:$E$11,"Víctor")+SUMIFS('Holgura'!$I$6:$I$11,'Holgura'!$B$6:$B$11,$A125,'Holgura'!$E$6:$E$11,"Ambos")+SUMIFS('Entrega'!$I$6:$I$9,'Entrega'!$B$6:$B$9,$A125,'Entrega'!$E$6:$E$9,"Víctor")+SUMIFS('Entrega'!$I$6:$I$9,'Entrega'!$B$6:$B$9,$A125,'Entrega'!$E$6:$E$9,"Ambos")+SUMIFS('Defensa'!$I$6:$I$10,'Defensa'!$B$6:$B$10,$A125,'Defensa'!$E$6:$E$10,"Víctor")+SUMIFS('Defensa'!$I$6:$I$10,'Defensa'!$B$6:$B$10,$A125,'Defensa'!$E$6:$E$10,"Ambos")</f>
+        <f>SUMIFS('S1'!$I$6:$I$32,'S1'!$B$6:$B$32,$A125,'S1'!$E$6:$E$32,"Víctor")+SUMIFS('S1'!$I$6:$I$32,'S1'!$B$6:$B$32,$A125,'S1'!$E$6:$E$32,"Ambos")+SUMIFS('S2'!$I$6:$I$23,'S2'!$B$6:$B$23,$A125,'S2'!$E$6:$E$23,"Víctor")+SUMIFS('S2'!$I$6:$I$23,'S2'!$B$6:$B$23,$A125,'S2'!$E$6:$E$23,"Ambos")+SUMIFS('S3'!$I$6:$I$24,'S3'!$B$6:$B$24,$A125,'S3'!$E$6:$E$24,"Víctor")+SUMIFS('S3'!$I$6:$I$24,'S3'!$B$6:$B$24,$A125,'S3'!$E$6:$E$24,"Ambos")+SUMIFS('S4'!$I$6:$I$22,'S4'!$B$6:$B$22,$A125,'S4'!$E$6:$E$22,"Víctor")+SUMIFS('S4'!$I$6:$I$22,'S4'!$B$6:$B$22,$A125,'S4'!$E$6:$E$22,"Ambos")+SUMIFS('S5'!$I$6:$I$20,'S5'!$B$6:$B$20,$A125,'S5'!$E$6:$E$20,"Víctor")+SUMIFS('S5'!$I$6:$I$20,'S5'!$B$6:$B$20,$A125,'S5'!$E$6:$E$20,"Ambos")+SUMIFS('S6'!$I$6:$I$17,'S6'!$B$6:$B$17,$A125,'S6'!$E$6:$E$17,"Víctor")+SUMIFS('S6'!$I$6:$I$17,'S6'!$B$6:$B$17,$A125,'S6'!$E$6:$E$17,"Ambos")+SUMIFS('S7'!$I$6:$I$19,'S7'!$B$6:$B$19,$A125,'S7'!$E$6:$E$19,"Víctor")+SUMIFS('S7'!$I$6:$I$19,'S7'!$B$6:$B$19,$A125,'S7'!$E$6:$E$19,"Ambos")+SUMIFS('S8'!$I$6:$I$23,'S8'!$B$6:$B$23,$A125,'S8'!$E$6:$E$23,"Víctor")+SUMIFS('S8'!$I$6:$I$23,'S8'!$B$6:$B$23,$A125,'S8'!$E$6:$E$23,"Ambos")+SUMIFS('S9'!$I$6:$I$15,'S9'!$B$6:$B$15,$A125,'S9'!$E$6:$E$15,"Víctor")+SUMIFS('S9'!$I$6:$I$15,'S9'!$B$6:$B$15,$A125,'S9'!$E$6:$E$15,"Ambos")+SUMIFS('S10'!$I$6:$I$13,'S10'!$B$6:$B$13,$A125,'S10'!$E$6:$E$13,"Víctor")+SUMIFS('S10'!$I$6:$I$13,'S10'!$B$6:$B$13,$A125,'S10'!$E$6:$E$13,"Ambos")+SUMIFS('Holgura'!$I$6:$I$11,'Holgura'!$B$6:$B$11,$A125,'Holgura'!$E$6:$E$11,"Víctor")+SUMIFS('Holgura'!$I$6:$I$11,'Holgura'!$B$6:$B$11,$A125,'Holgura'!$E$6:$E$11,"Ambos")+SUMIFS('Entrega'!$I$6:$I$9,'Entrega'!$B$6:$B$9,$A125,'Entrega'!$E$6:$E$9,"Víctor")+SUMIFS('Entrega'!$I$6:$I$9,'Entrega'!$B$6:$B$9,$A125,'Entrega'!$E$6:$E$9,"Ambos")+SUMIFS('Defensa'!$I$6:$I$10,'Defensa'!$B$6:$B$10,$A125,'Defensa'!$E$6:$E$10,"Víctor")+SUMIFS('Defensa'!$I$6:$I$10,'Defensa'!$B$6:$B$10,$A125,'Defensa'!$E$6:$E$10,"Ambos")</f>
         <v/>
       </c>
       <c r="E125" s="21">
-        <f>SUMIFS('S1'!$I$6:$I$32,'S1'!$B$6:$B$32,$A125,'S1'!$E$6:$E$32,"Diego")+SUMIFS('S1'!$I$6:$I$32,'S1'!$B$6:$B$32,$A125,'S1'!$E$6:$E$32,"Ambos")+SUMIFS('S2'!$I$6:$I$23,'S2'!$B$6:$B$23,$A125,'S2'!$E$6:$E$23,"Diego")+SUMIFS('S2'!$I$6:$I$23,'S2'!$B$6:$B$23,$A125,'S2'!$E$6:$E$23,"Ambos")+SUMIFS('S3'!$I$6:$I$19,'S3'!$B$6:$B$19,$A125,'S3'!$E$6:$E$19,"Diego")+SUMIFS('S3'!$I$6:$I$19,'S3'!$B$6:$B$19,$A125,'S3'!$E$6:$E$19,"Ambos")+SUMIFS('S4'!$I$6:$I$20,'S4'!$B$6:$B$20,$A125,'S4'!$E$6:$E$20,"Diego")+SUMIFS('S4'!$I$6:$I$20,'S4'!$B$6:$B$20,$A125,'S4'!$E$6:$E$20,"Ambos")+SUMIFS('S5'!$I$6:$I$20,'S5'!$B$6:$B$20,$A125,'S5'!$E$6:$E$20,"Diego")+SUMIFS('S5'!$I$6:$I$20,'S5'!$B$6:$B$20,$A125,'S5'!$E$6:$E$20,"Ambos")+SUMIFS('S6'!$I$6:$I$17,'S6'!$B$6:$B$17,$A125,'S6'!$E$6:$E$17,"Diego")+SUMIFS('S6'!$I$6:$I$17,'S6'!$B$6:$B$17,$A125,'S6'!$E$6:$E$17,"Ambos")+SUMIFS('S7'!$I$6:$I$19,'S7'!$B$6:$B$19,$A125,'S7'!$E$6:$E$19,"Diego")+SUMIFS('S7'!$I$6:$I$19,'S7'!$B$6:$B$19,$A125,'S7'!$E$6:$E$19,"Ambos")+SUMIFS('S8'!$I$6:$I$23,'S8'!$B$6:$B$23,$A125,'S8'!$E$6:$E$23,"Diego")+SUMIFS('S8'!$I$6:$I$23,'S8'!$B$6:$B$23,$A125,'S8'!$E$6:$E$23,"Ambos")+SUMIFS('S9'!$I$6:$I$15,'S9'!$B$6:$B$15,$A125,'S9'!$E$6:$E$15,"Diego")+SUMIFS('S9'!$I$6:$I$15,'S9'!$B$6:$B$15,$A125,'S9'!$E$6:$E$15,"Ambos")+SUMIFS('S10'!$I$6:$I$13,'S10'!$B$6:$B$13,$A125,'S10'!$E$6:$E$13,"Diego")+SUMIFS('S10'!$I$6:$I$13,'S10'!$B$6:$B$13,$A125,'S10'!$E$6:$E$13,"Ambos")+SUMIFS('Holgura'!$I$6:$I$11,'Holgura'!$B$6:$B$11,$A125,'Holgura'!$E$6:$E$11,"Diego")+SUMIFS('Holgura'!$I$6:$I$11,'Holgura'!$B$6:$B$11,$A125,'Holgura'!$E$6:$E$11,"Ambos")+SUMIFS('Entrega'!$I$6:$I$9,'Entrega'!$B$6:$B$9,$A125,'Entrega'!$E$6:$E$9,"Diego")+SUMIFS('Entrega'!$I$6:$I$9,'Entrega'!$B$6:$B$9,$A125,'Entrega'!$E$6:$E$9,"Ambos")+SUMIFS('Defensa'!$I$6:$I$10,'Defensa'!$B$6:$B$10,$A125,'Defensa'!$E$6:$E$10,"Diego")+SUMIFS('Defensa'!$I$6:$I$10,'Defensa'!$B$6:$B$10,$A125,'Defensa'!$E$6:$E$10,"Ambos")</f>
+        <f>SUMIFS('S1'!$I$6:$I$32,'S1'!$B$6:$B$32,$A125,'S1'!$E$6:$E$32,"Diego")+SUMIFS('S1'!$I$6:$I$32,'S1'!$B$6:$B$32,$A125,'S1'!$E$6:$E$32,"Ambos")+SUMIFS('S2'!$I$6:$I$23,'S2'!$B$6:$B$23,$A125,'S2'!$E$6:$E$23,"Diego")+SUMIFS('S2'!$I$6:$I$23,'S2'!$B$6:$B$23,$A125,'S2'!$E$6:$E$23,"Ambos")+SUMIFS('S3'!$I$6:$I$24,'S3'!$B$6:$B$24,$A125,'S3'!$E$6:$E$24,"Diego")+SUMIFS('S3'!$I$6:$I$24,'S3'!$B$6:$B$24,$A125,'S3'!$E$6:$E$24,"Ambos")+SUMIFS('S4'!$I$6:$I$22,'S4'!$B$6:$B$22,$A125,'S4'!$E$6:$E$22,"Diego")+SUMIFS('S4'!$I$6:$I$22,'S4'!$B$6:$B$22,$A125,'S4'!$E$6:$E$22,"Ambos")+SUMIFS('S5'!$I$6:$I$20,'S5'!$B$6:$B$20,$A125,'S5'!$E$6:$E$20,"Diego")+SUMIFS('S5'!$I$6:$I$20,'S5'!$B$6:$B$20,$A125,'S5'!$E$6:$E$20,"Ambos")+SUMIFS('S6'!$I$6:$I$17,'S6'!$B$6:$B$17,$A125,'S6'!$E$6:$E$17,"Diego")+SUMIFS('S6'!$I$6:$I$17,'S6'!$B$6:$B$17,$A125,'S6'!$E$6:$E$17,"Ambos")+SUMIFS('S7'!$I$6:$I$19,'S7'!$B$6:$B$19,$A125,'S7'!$E$6:$E$19,"Diego")+SUMIFS('S7'!$I$6:$I$19,'S7'!$B$6:$B$19,$A125,'S7'!$E$6:$E$19,"Ambos")+SUMIFS('S8'!$I$6:$I$23,'S8'!$B$6:$B$23,$A125,'S8'!$E$6:$E$23,"Diego")+SUMIFS('S8'!$I$6:$I$23,'S8'!$B$6:$B$23,$A125,'S8'!$E$6:$E$23,"Ambos")+SUMIFS('S9'!$I$6:$I$15,'S9'!$B$6:$B$15,$A125,'S9'!$E$6:$E$15,"Diego")+SUMIFS('S9'!$I$6:$I$15,'S9'!$B$6:$B$15,$A125,'S9'!$E$6:$E$15,"Ambos")+SUMIFS('S10'!$I$6:$I$13,'S10'!$B$6:$B$13,$A125,'S10'!$E$6:$E$13,"Diego")+SUMIFS('S10'!$I$6:$I$13,'S10'!$B$6:$B$13,$A125,'S10'!$E$6:$E$13,"Ambos")+SUMIFS('Holgura'!$I$6:$I$11,'Holgura'!$B$6:$B$11,$A125,'Holgura'!$E$6:$E$11,"Diego")+SUMIFS('Holgura'!$I$6:$I$11,'Holgura'!$B$6:$B$11,$A125,'Holgura'!$E$6:$E$11,"Ambos")+SUMIFS('Entrega'!$I$6:$I$9,'Entrega'!$B$6:$B$9,$A125,'Entrega'!$E$6:$E$9,"Diego")+SUMIFS('Entrega'!$I$6:$I$9,'Entrega'!$B$6:$B$9,$A125,'Entrega'!$E$6:$E$9,"Ambos")+SUMIFS('Defensa'!$I$6:$I$10,'Defensa'!$B$6:$B$10,$A125,'Defensa'!$E$6:$E$10,"Diego")+SUMIFS('Defensa'!$I$6:$I$10,'Defensa'!$B$6:$B$10,$A125,'Defensa'!$E$6:$E$10,"Ambos")</f>
         <v/>
       </c>
       <c r="F125" s="21">
-        <f>COUNTIFS('S1'!$B$6:$B$32,$A125,'S1'!$E$6:$E$32,"Víctor")+COUNTIFS('S1'!$B$6:$B$32,$A125,'S1'!$E$6:$E$32,"Ambos")+COUNTIFS('S2'!$B$6:$B$23,$A125,'S2'!$E$6:$E$23,"Víctor")+COUNTIFS('S2'!$B$6:$B$23,$A125,'S2'!$E$6:$E$23,"Ambos")+COUNTIFS('S3'!$B$6:$B$19,$A125,'S3'!$E$6:$E$19,"Víctor")+COUNTIFS('S3'!$B$6:$B$19,$A125,'S3'!$E$6:$E$19,"Ambos")+COUNTIFS('S4'!$B$6:$B$20,$A125,'S4'!$E$6:$E$20,"Víctor")+COUNTIFS('S4'!$B$6:$B$20,$A125,'S4'!$E$6:$E$20,"Ambos")+COUNTIFS('S5'!$B$6:$B$20,$A125,'S5'!$E$6:$E$20,"Víctor")+COUNTIFS('S5'!$B$6:$B$20,$A125,'S5'!$E$6:$E$20,"Ambos")+COUNTIFS('S6'!$B$6:$B$17,$A125,'S6'!$E$6:$E$17,"Víctor")+COUNTIFS('S6'!$B$6:$B$17,$A125,'S6'!$E$6:$E$17,"Ambos")+COUNTIFS('S7'!$B$6:$B$19,$A125,'S7'!$E$6:$E$19,"Víctor")+COUNTIFS('S7'!$B$6:$B$19,$A125,'S7'!$E$6:$E$19,"Ambos")+COUNTIFS('S8'!$B$6:$B$23,$A125,'S8'!$E$6:$E$23,"Víctor")+COUNTIFS('S8'!$B$6:$B$23,$A125,'S8'!$E$6:$E$23,"Ambos")+COUNTIFS('S9'!$B$6:$B$15,$A125,'S9'!$E$6:$E$15,"Víctor")+COUNTIFS('S9'!$B$6:$B$15,$A125,'S9'!$E$6:$E$15,"Ambos")+COUNTIFS('S10'!$B$6:$B$13,$A125,'S10'!$E$6:$E$13,"Víctor")+COUNTIFS('S10'!$B$6:$B$13,$A125,'S10'!$E$6:$E$13,"Ambos")+COUNTIFS('Holgura'!$B$6:$B$11,$A125,'Holgura'!$E$6:$E$11,"Víctor")+COUNTIFS('Holgura'!$B$6:$B$11,$A125,'Holgura'!$E$6:$E$11,"Ambos")+COUNTIFS('Entrega'!$B$6:$B$9,$A125,'Entrega'!$E$6:$E$9,"Víctor")+COUNTIFS('Entrega'!$B$6:$B$9,$A125,'Entrega'!$E$6:$E$9,"Ambos")+COUNTIFS('Defensa'!$B$6:$B$10,$A125,'Defensa'!$E$6:$E$10,"Víctor")+COUNTIFS('Defensa'!$B$6:$B$10,$A125,'Defensa'!$E$6:$E$10,"Ambos")</f>
+        <f>COUNTIFS('S1'!$B$6:$B$32,$A125,'S1'!$E$6:$E$32,"Víctor")+COUNTIFS('S1'!$B$6:$B$32,$A125,'S1'!$E$6:$E$32,"Ambos")+COUNTIFS('S2'!$B$6:$B$23,$A125,'S2'!$E$6:$E$23,"Víctor")+COUNTIFS('S2'!$B$6:$B$23,$A125,'S2'!$E$6:$E$23,"Ambos")+COUNTIFS('S3'!$B$6:$B$24,$A125,'S3'!$E$6:$E$24,"Víctor")+COUNTIFS('S3'!$B$6:$B$24,$A125,'S3'!$E$6:$E$24,"Ambos")+COUNTIFS('S4'!$B$6:$B$22,$A125,'S4'!$E$6:$E$22,"Víctor")+COUNTIFS('S4'!$B$6:$B$22,$A125,'S4'!$E$6:$E$22,"Ambos")+COUNTIFS('S5'!$B$6:$B$20,$A125,'S5'!$E$6:$E$20,"Víctor")+COUNTIFS('S5'!$B$6:$B$20,$A125,'S5'!$E$6:$E$20,"Ambos")+COUNTIFS('S6'!$B$6:$B$17,$A125,'S6'!$E$6:$E$17,"Víctor")+COUNTIFS('S6'!$B$6:$B$17,$A125,'S6'!$E$6:$E$17,"Ambos")+COUNTIFS('S7'!$B$6:$B$19,$A125,'S7'!$E$6:$E$19,"Víctor")+COUNTIFS('S7'!$B$6:$B$19,$A125,'S7'!$E$6:$E$19,"Ambos")+COUNTIFS('S8'!$B$6:$B$23,$A125,'S8'!$E$6:$E$23,"Víctor")+COUNTIFS('S8'!$B$6:$B$23,$A125,'S8'!$E$6:$E$23,"Ambos")+COUNTIFS('S9'!$B$6:$B$15,$A125,'S9'!$E$6:$E$15,"Víctor")+COUNTIFS('S9'!$B$6:$B$15,$A125,'S9'!$E$6:$E$15,"Ambos")+COUNTIFS('S10'!$B$6:$B$13,$A125,'S10'!$E$6:$E$13,"Víctor")+COUNTIFS('S10'!$B$6:$B$13,$A125,'S10'!$E$6:$E$13,"Ambos")+COUNTIFS('Holgura'!$B$6:$B$11,$A125,'Holgura'!$E$6:$E$11,"Víctor")+COUNTIFS('Holgura'!$B$6:$B$11,$A125,'Holgura'!$E$6:$E$11,"Ambos")+COUNTIFS('Entrega'!$B$6:$B$9,$A125,'Entrega'!$E$6:$E$9,"Víctor")+COUNTIFS('Entrega'!$B$6:$B$9,$A125,'Entrega'!$E$6:$E$9,"Ambos")+COUNTIFS('Defensa'!$B$6:$B$10,$A125,'Defensa'!$E$6:$E$10,"Víctor")+COUNTIFS('Defensa'!$B$6:$B$10,$A125,'Defensa'!$E$6:$E$10,"Ambos")</f>
         <v/>
       </c>
       <c r="G125" s="21">
-        <f>COUNTIFS('S1'!$B$6:$B$32,$A125,'S1'!$E$6:$E$32,"Diego")+COUNTIFS('S1'!$B$6:$B$32,$A125,'S1'!$E$6:$E$32,"Ambos")+COUNTIFS('S2'!$B$6:$B$23,$A125,'S2'!$E$6:$E$23,"Diego")+COUNTIFS('S2'!$B$6:$B$23,$A125,'S2'!$E$6:$E$23,"Ambos")+COUNTIFS('S3'!$B$6:$B$19,$A125,'S3'!$E$6:$E$19,"Diego")+COUNTIFS('S3'!$B$6:$B$19,$A125,'S3'!$E$6:$E$19,"Ambos")+COUNTIFS('S4'!$B$6:$B$20,$A125,'S4'!$E$6:$E$20,"Diego")+COUNTIFS('S4'!$B$6:$B$20,$A125,'S4'!$E$6:$E$20,"Ambos")+COUNTIFS('S5'!$B$6:$B$20,$A125,'S5'!$E$6:$E$20,"Diego")+COUNTIFS('S5'!$B$6:$B$20,$A125,'S5'!$E$6:$E$20,"Ambos")+COUNTIFS('S6'!$B$6:$B$17,$A125,'S6'!$E$6:$E$17,"Diego")+COUNTIFS('S6'!$B$6:$B$17,$A125,'S6'!$E$6:$E$17,"Ambos")+COUNTIFS('S7'!$B$6:$B$19,$A125,'S7'!$E$6:$E$19,"Diego")+COUNTIFS('S7'!$B$6:$B$19,$A125,'S7'!$E$6:$E$19,"Ambos")+COUNTIFS('S8'!$B$6:$B$23,$A125,'S8'!$E$6:$E$23,"Diego")+COUNTIFS('S8'!$B$6:$B$23,$A125,'S8'!$E$6:$E$23,"Ambos")+COUNTIFS('S9'!$B$6:$B$15,$A125,'S9'!$E$6:$E$15,"Diego")+COUNTIFS('S9'!$B$6:$B$15,$A125,'S9'!$E$6:$E$15,"Ambos")+COUNTIFS('S10'!$B$6:$B$13,$A125,'S10'!$E$6:$E$13,"Diego")+COUNTIFS('S10'!$B$6:$B$13,$A125,'S10'!$E$6:$E$13,"Ambos")+COUNTIFS('Holgura'!$B$6:$B$11,$A125,'Holgura'!$E$6:$E$11,"Diego")+COUNTIFS('Holgura'!$B$6:$B$11,$A125,'Holgura'!$E$6:$E$11,"Ambos")+COUNTIFS('Entrega'!$B$6:$B$9,$A125,'Entrega'!$E$6:$E$9,"Diego")+COUNTIFS('Entrega'!$B$6:$B$9,$A125,'Entrega'!$E$6:$E$9,"Ambos")+COUNTIFS('Defensa'!$B$6:$B$10,$A125,'Defensa'!$E$6:$E$10,"Diego")+COUNTIFS('Defensa'!$B$6:$B$10,$A125,'Defensa'!$E$6:$E$10,"Ambos")</f>
+        <f>COUNTIFS('S1'!$B$6:$B$32,$A125,'S1'!$E$6:$E$32,"Diego")+COUNTIFS('S1'!$B$6:$B$32,$A125,'S1'!$E$6:$E$32,"Ambos")+COUNTIFS('S2'!$B$6:$B$23,$A125,'S2'!$E$6:$E$23,"Diego")+COUNTIFS('S2'!$B$6:$B$23,$A125,'S2'!$E$6:$E$23,"Ambos")+COUNTIFS('S3'!$B$6:$B$24,$A125,'S3'!$E$6:$E$24,"Diego")+COUNTIFS('S3'!$B$6:$B$24,$A125,'S3'!$E$6:$E$24,"Ambos")+COUNTIFS('S4'!$B$6:$B$22,$A125,'S4'!$E$6:$E$22,"Diego")+COUNTIFS('S4'!$B$6:$B$22,$A125,'S4'!$E$6:$E$22,"Ambos")+COUNTIFS('S5'!$B$6:$B$20,$A125,'S5'!$E$6:$E$20,"Diego")+COUNTIFS('S5'!$B$6:$B$20,$A125,'S5'!$E$6:$E$20,"Ambos")+COUNTIFS('S6'!$B$6:$B$17,$A125,'S6'!$E$6:$E$17,"Diego")+COUNTIFS('S6'!$B$6:$B$17,$A125,'S6'!$E$6:$E$17,"Ambos")+COUNTIFS('S7'!$B$6:$B$19,$A125,'S7'!$E$6:$E$19,"Diego")+COUNTIFS('S7'!$B$6:$B$19,$A125,'S7'!$E$6:$E$19,"Ambos")+COUNTIFS('S8'!$B$6:$B$23,$A125,'S8'!$E$6:$E$23,"Diego")+COUNTIFS('S8'!$B$6:$B$23,$A125,'S8'!$E$6:$E$23,"Ambos")+COUNTIFS('S9'!$B$6:$B$15,$A125,'S9'!$E$6:$E$15,"Diego")+COUNTIFS('S9'!$B$6:$B$15,$A125,'S9'!$E$6:$E$15,"Ambos")+COUNTIFS('S10'!$B$6:$B$13,$A125,'S10'!$E$6:$E$13,"Diego")+COUNTIFS('S10'!$B$6:$B$13,$A125,'S10'!$E$6:$E$13,"Ambos")+COUNTIFS('Holgura'!$B$6:$B$11,$A125,'Holgura'!$E$6:$E$11,"Diego")+COUNTIFS('Holgura'!$B$6:$B$11,$A125,'Holgura'!$E$6:$E$11,"Ambos")+COUNTIFS('Entrega'!$B$6:$B$9,$A125,'Entrega'!$E$6:$E$9,"Diego")+COUNTIFS('Entrega'!$B$6:$B$9,$A125,'Entrega'!$E$6:$E$9,"Ambos")+COUNTIFS('Defensa'!$B$6:$B$10,$A125,'Defensa'!$E$6:$E$10,"Diego")+COUNTIFS('Defensa'!$B$6:$B$10,$A125,'Defensa'!$E$6:$E$10,"Ambos")</f>
         <v/>
       </c>
     </row>
@@ -12189,19 +12210,19 @@
         <v/>
       </c>
       <c r="D126" s="21">
-        <f>SUMIFS('S1'!$I$6:$I$32,'S1'!$B$6:$B$32,$A126,'S1'!$E$6:$E$32,"Víctor")+SUMIFS('S1'!$I$6:$I$32,'S1'!$B$6:$B$32,$A126,'S1'!$E$6:$E$32,"Ambos")+SUMIFS('S2'!$I$6:$I$23,'S2'!$B$6:$B$23,$A126,'S2'!$E$6:$E$23,"Víctor")+SUMIFS('S2'!$I$6:$I$23,'S2'!$B$6:$B$23,$A126,'S2'!$E$6:$E$23,"Ambos")+SUMIFS('S3'!$I$6:$I$19,'S3'!$B$6:$B$19,$A126,'S3'!$E$6:$E$19,"Víctor")+SUMIFS('S3'!$I$6:$I$19,'S3'!$B$6:$B$19,$A126,'S3'!$E$6:$E$19,"Ambos")+SUMIFS('S4'!$I$6:$I$20,'S4'!$B$6:$B$20,$A126,'S4'!$E$6:$E$20,"Víctor")+SUMIFS('S4'!$I$6:$I$20,'S4'!$B$6:$B$20,$A126,'S4'!$E$6:$E$20,"Ambos")+SUMIFS('S5'!$I$6:$I$20,'S5'!$B$6:$B$20,$A126,'S5'!$E$6:$E$20,"Víctor")+SUMIFS('S5'!$I$6:$I$20,'S5'!$B$6:$B$20,$A126,'S5'!$E$6:$E$20,"Ambos")+SUMIFS('S6'!$I$6:$I$17,'S6'!$B$6:$B$17,$A126,'S6'!$E$6:$E$17,"Víctor")+SUMIFS('S6'!$I$6:$I$17,'S6'!$B$6:$B$17,$A126,'S6'!$E$6:$E$17,"Ambos")+SUMIFS('S7'!$I$6:$I$19,'S7'!$B$6:$B$19,$A126,'S7'!$E$6:$E$19,"Víctor")+SUMIFS('S7'!$I$6:$I$19,'S7'!$B$6:$B$19,$A126,'S7'!$E$6:$E$19,"Ambos")+SUMIFS('S8'!$I$6:$I$23,'S8'!$B$6:$B$23,$A126,'S8'!$E$6:$E$23,"Víctor")+SUMIFS('S8'!$I$6:$I$23,'S8'!$B$6:$B$23,$A126,'S8'!$E$6:$E$23,"Ambos")+SUMIFS('S9'!$I$6:$I$15,'S9'!$B$6:$B$15,$A126,'S9'!$E$6:$E$15,"Víctor")+SUMIFS('S9'!$I$6:$I$15,'S9'!$B$6:$B$15,$A126,'S9'!$E$6:$E$15,"Ambos")+SUMIFS('S10'!$I$6:$I$13,'S10'!$B$6:$B$13,$A126,'S10'!$E$6:$E$13,"Víctor")+SUMIFS('S10'!$I$6:$I$13,'S10'!$B$6:$B$13,$A126,'S10'!$E$6:$E$13,"Ambos")+SUMIFS('Holgura'!$I$6:$I$11,'Holgura'!$B$6:$B$11,$A126,'Holgura'!$E$6:$E$11,"Víctor")+SUMIFS('Holgura'!$I$6:$I$11,'Holgura'!$B$6:$B$11,$A126,'Holgura'!$E$6:$E$11,"Ambos")+SUMIFS('Entrega'!$I$6:$I$9,'Entrega'!$B$6:$B$9,$A126,'Entrega'!$E$6:$E$9,"Víctor")+SUMIFS('Entrega'!$I$6:$I$9,'Entrega'!$B$6:$B$9,$A126,'Entrega'!$E$6:$E$9,"Ambos")+SUMIFS('Defensa'!$I$6:$I$10,'Defensa'!$B$6:$B$10,$A126,'Defensa'!$E$6:$E$10,"Víctor")+SUMIFS('Defensa'!$I$6:$I$10,'Defensa'!$B$6:$B$10,$A126,'Defensa'!$E$6:$E$10,"Ambos")</f>
+        <f>SUMIFS('S1'!$I$6:$I$32,'S1'!$B$6:$B$32,$A126,'S1'!$E$6:$E$32,"Víctor")+SUMIFS('S1'!$I$6:$I$32,'S1'!$B$6:$B$32,$A126,'S1'!$E$6:$E$32,"Ambos")+SUMIFS('S2'!$I$6:$I$23,'S2'!$B$6:$B$23,$A126,'S2'!$E$6:$E$23,"Víctor")+SUMIFS('S2'!$I$6:$I$23,'S2'!$B$6:$B$23,$A126,'S2'!$E$6:$E$23,"Ambos")+SUMIFS('S3'!$I$6:$I$24,'S3'!$B$6:$B$24,$A126,'S3'!$E$6:$E$24,"Víctor")+SUMIFS('S3'!$I$6:$I$24,'S3'!$B$6:$B$24,$A126,'S3'!$E$6:$E$24,"Ambos")+SUMIFS('S4'!$I$6:$I$22,'S4'!$B$6:$B$22,$A126,'S4'!$E$6:$E$22,"Víctor")+SUMIFS('S4'!$I$6:$I$22,'S4'!$B$6:$B$22,$A126,'S4'!$E$6:$E$22,"Ambos")+SUMIFS('S5'!$I$6:$I$20,'S5'!$B$6:$B$20,$A126,'S5'!$E$6:$E$20,"Víctor")+SUMIFS('S5'!$I$6:$I$20,'S5'!$B$6:$B$20,$A126,'S5'!$E$6:$E$20,"Ambos")+SUMIFS('S6'!$I$6:$I$17,'S6'!$B$6:$B$17,$A126,'S6'!$E$6:$E$17,"Víctor")+SUMIFS('S6'!$I$6:$I$17,'S6'!$B$6:$B$17,$A126,'S6'!$E$6:$E$17,"Ambos")+SUMIFS('S7'!$I$6:$I$19,'S7'!$B$6:$B$19,$A126,'S7'!$E$6:$E$19,"Víctor")+SUMIFS('S7'!$I$6:$I$19,'S7'!$B$6:$B$19,$A126,'S7'!$E$6:$E$19,"Ambos")+SUMIFS('S8'!$I$6:$I$23,'S8'!$B$6:$B$23,$A126,'S8'!$E$6:$E$23,"Víctor")+SUMIFS('S8'!$I$6:$I$23,'S8'!$B$6:$B$23,$A126,'S8'!$E$6:$E$23,"Ambos")+SUMIFS('S9'!$I$6:$I$15,'S9'!$B$6:$B$15,$A126,'S9'!$E$6:$E$15,"Víctor")+SUMIFS('S9'!$I$6:$I$15,'S9'!$B$6:$B$15,$A126,'S9'!$E$6:$E$15,"Ambos")+SUMIFS('S10'!$I$6:$I$13,'S10'!$B$6:$B$13,$A126,'S10'!$E$6:$E$13,"Víctor")+SUMIFS('S10'!$I$6:$I$13,'S10'!$B$6:$B$13,$A126,'S10'!$E$6:$E$13,"Ambos")+SUMIFS('Holgura'!$I$6:$I$11,'Holgura'!$B$6:$B$11,$A126,'Holgura'!$E$6:$E$11,"Víctor")+SUMIFS('Holgura'!$I$6:$I$11,'Holgura'!$B$6:$B$11,$A126,'Holgura'!$E$6:$E$11,"Ambos")+SUMIFS('Entrega'!$I$6:$I$9,'Entrega'!$B$6:$B$9,$A126,'Entrega'!$E$6:$E$9,"Víctor")+SUMIFS('Entrega'!$I$6:$I$9,'Entrega'!$B$6:$B$9,$A126,'Entrega'!$E$6:$E$9,"Ambos")+SUMIFS('Defensa'!$I$6:$I$10,'Defensa'!$B$6:$B$10,$A126,'Defensa'!$E$6:$E$10,"Víctor")+SUMIFS('Defensa'!$I$6:$I$10,'Defensa'!$B$6:$B$10,$A126,'Defensa'!$E$6:$E$10,"Ambos")</f>
         <v/>
       </c>
       <c r="E126" s="21">
-        <f>SUMIFS('S1'!$I$6:$I$32,'S1'!$B$6:$B$32,$A126,'S1'!$E$6:$E$32,"Diego")+SUMIFS('S1'!$I$6:$I$32,'S1'!$B$6:$B$32,$A126,'S1'!$E$6:$E$32,"Ambos")+SUMIFS('S2'!$I$6:$I$23,'S2'!$B$6:$B$23,$A126,'S2'!$E$6:$E$23,"Diego")+SUMIFS('S2'!$I$6:$I$23,'S2'!$B$6:$B$23,$A126,'S2'!$E$6:$E$23,"Ambos")+SUMIFS('S3'!$I$6:$I$19,'S3'!$B$6:$B$19,$A126,'S3'!$E$6:$E$19,"Diego")+SUMIFS('S3'!$I$6:$I$19,'S3'!$B$6:$B$19,$A126,'S3'!$E$6:$E$19,"Ambos")+SUMIFS('S4'!$I$6:$I$20,'S4'!$B$6:$B$20,$A126,'S4'!$E$6:$E$20,"Diego")+SUMIFS('S4'!$I$6:$I$20,'S4'!$B$6:$B$20,$A126,'S4'!$E$6:$E$20,"Ambos")+SUMIFS('S5'!$I$6:$I$20,'S5'!$B$6:$B$20,$A126,'S5'!$E$6:$E$20,"Diego")+SUMIFS('S5'!$I$6:$I$20,'S5'!$B$6:$B$20,$A126,'S5'!$E$6:$E$20,"Ambos")+SUMIFS('S6'!$I$6:$I$17,'S6'!$B$6:$B$17,$A126,'S6'!$E$6:$E$17,"Diego")+SUMIFS('S6'!$I$6:$I$17,'S6'!$B$6:$B$17,$A126,'S6'!$E$6:$E$17,"Ambos")+SUMIFS('S7'!$I$6:$I$19,'S7'!$B$6:$B$19,$A126,'S7'!$E$6:$E$19,"Diego")+SUMIFS('S7'!$I$6:$I$19,'S7'!$B$6:$B$19,$A126,'S7'!$E$6:$E$19,"Ambos")+SUMIFS('S8'!$I$6:$I$23,'S8'!$B$6:$B$23,$A126,'S8'!$E$6:$E$23,"Diego")+SUMIFS('S8'!$I$6:$I$23,'S8'!$B$6:$B$23,$A126,'S8'!$E$6:$E$23,"Ambos")+SUMIFS('S9'!$I$6:$I$15,'S9'!$B$6:$B$15,$A126,'S9'!$E$6:$E$15,"Diego")+SUMIFS('S9'!$I$6:$I$15,'S9'!$B$6:$B$15,$A126,'S9'!$E$6:$E$15,"Ambos")+SUMIFS('S10'!$I$6:$I$13,'S10'!$B$6:$B$13,$A126,'S10'!$E$6:$E$13,"Diego")+SUMIFS('S10'!$I$6:$I$13,'S10'!$B$6:$B$13,$A126,'S10'!$E$6:$E$13,"Ambos")+SUMIFS('Holgura'!$I$6:$I$11,'Holgura'!$B$6:$B$11,$A126,'Holgura'!$E$6:$E$11,"Diego")+SUMIFS('Holgura'!$I$6:$I$11,'Holgura'!$B$6:$B$11,$A126,'Holgura'!$E$6:$E$11,"Ambos")+SUMIFS('Entrega'!$I$6:$I$9,'Entrega'!$B$6:$B$9,$A126,'Entrega'!$E$6:$E$9,"Diego")+SUMIFS('Entrega'!$I$6:$I$9,'Entrega'!$B$6:$B$9,$A126,'Entrega'!$E$6:$E$9,"Ambos")+SUMIFS('Defensa'!$I$6:$I$10,'Defensa'!$B$6:$B$10,$A126,'Defensa'!$E$6:$E$10,"Diego")+SUMIFS('Defensa'!$I$6:$I$10,'Defensa'!$B$6:$B$10,$A126,'Defensa'!$E$6:$E$10,"Ambos")</f>
+        <f>SUMIFS('S1'!$I$6:$I$32,'S1'!$B$6:$B$32,$A126,'S1'!$E$6:$E$32,"Diego")+SUMIFS('S1'!$I$6:$I$32,'S1'!$B$6:$B$32,$A126,'S1'!$E$6:$E$32,"Ambos")+SUMIFS('S2'!$I$6:$I$23,'S2'!$B$6:$B$23,$A126,'S2'!$E$6:$E$23,"Diego")+SUMIFS('S2'!$I$6:$I$23,'S2'!$B$6:$B$23,$A126,'S2'!$E$6:$E$23,"Ambos")+SUMIFS('S3'!$I$6:$I$24,'S3'!$B$6:$B$24,$A126,'S3'!$E$6:$E$24,"Diego")+SUMIFS('S3'!$I$6:$I$24,'S3'!$B$6:$B$24,$A126,'S3'!$E$6:$E$24,"Ambos")+SUMIFS('S4'!$I$6:$I$22,'S4'!$B$6:$B$22,$A126,'S4'!$E$6:$E$22,"Diego")+SUMIFS('S4'!$I$6:$I$22,'S4'!$B$6:$B$22,$A126,'S4'!$E$6:$E$22,"Ambos")+SUMIFS('S5'!$I$6:$I$20,'S5'!$B$6:$B$20,$A126,'S5'!$E$6:$E$20,"Diego")+SUMIFS('S5'!$I$6:$I$20,'S5'!$B$6:$B$20,$A126,'S5'!$E$6:$E$20,"Ambos")+SUMIFS('S6'!$I$6:$I$17,'S6'!$B$6:$B$17,$A126,'S6'!$E$6:$E$17,"Diego")+SUMIFS('S6'!$I$6:$I$17,'S6'!$B$6:$B$17,$A126,'S6'!$E$6:$E$17,"Ambos")+SUMIFS('S7'!$I$6:$I$19,'S7'!$B$6:$B$19,$A126,'S7'!$E$6:$E$19,"Diego")+SUMIFS('S7'!$I$6:$I$19,'S7'!$B$6:$B$19,$A126,'S7'!$E$6:$E$19,"Ambos")+SUMIFS('S8'!$I$6:$I$23,'S8'!$B$6:$B$23,$A126,'S8'!$E$6:$E$23,"Diego")+SUMIFS('S8'!$I$6:$I$23,'S8'!$B$6:$B$23,$A126,'S8'!$E$6:$E$23,"Ambos")+SUMIFS('S9'!$I$6:$I$15,'S9'!$B$6:$B$15,$A126,'S9'!$E$6:$E$15,"Diego")+SUMIFS('S9'!$I$6:$I$15,'S9'!$B$6:$B$15,$A126,'S9'!$E$6:$E$15,"Ambos")+SUMIFS('S10'!$I$6:$I$13,'S10'!$B$6:$B$13,$A126,'S10'!$E$6:$E$13,"Diego")+SUMIFS('S10'!$I$6:$I$13,'S10'!$B$6:$B$13,$A126,'S10'!$E$6:$E$13,"Ambos")+SUMIFS('Holgura'!$I$6:$I$11,'Holgura'!$B$6:$B$11,$A126,'Holgura'!$E$6:$E$11,"Diego")+SUMIFS('Holgura'!$I$6:$I$11,'Holgura'!$B$6:$B$11,$A126,'Holgura'!$E$6:$E$11,"Ambos")+SUMIFS('Entrega'!$I$6:$I$9,'Entrega'!$B$6:$B$9,$A126,'Entrega'!$E$6:$E$9,"Diego")+SUMIFS('Entrega'!$I$6:$I$9,'Entrega'!$B$6:$B$9,$A126,'Entrega'!$E$6:$E$9,"Ambos")+SUMIFS('Defensa'!$I$6:$I$10,'Defensa'!$B$6:$B$10,$A126,'Defensa'!$E$6:$E$10,"Diego")+SUMIFS('Defensa'!$I$6:$I$10,'Defensa'!$B$6:$B$10,$A126,'Defensa'!$E$6:$E$10,"Ambos")</f>
         <v/>
       </c>
       <c r="F126" s="21">
-        <f>COUNTIFS('S1'!$B$6:$B$32,$A126,'S1'!$E$6:$E$32,"Víctor")+COUNTIFS('S1'!$B$6:$B$32,$A126,'S1'!$E$6:$E$32,"Ambos")+COUNTIFS('S2'!$B$6:$B$23,$A126,'S2'!$E$6:$E$23,"Víctor")+COUNTIFS('S2'!$B$6:$B$23,$A126,'S2'!$E$6:$E$23,"Ambos")+COUNTIFS('S3'!$B$6:$B$19,$A126,'S3'!$E$6:$E$19,"Víctor")+COUNTIFS('S3'!$B$6:$B$19,$A126,'S3'!$E$6:$E$19,"Ambos")+COUNTIFS('S4'!$B$6:$B$20,$A126,'S4'!$E$6:$E$20,"Víctor")+COUNTIFS('S4'!$B$6:$B$20,$A126,'S4'!$E$6:$E$20,"Ambos")+COUNTIFS('S5'!$B$6:$B$20,$A126,'S5'!$E$6:$E$20,"Víctor")+COUNTIFS('S5'!$B$6:$B$20,$A126,'S5'!$E$6:$E$20,"Ambos")+COUNTIFS('S6'!$B$6:$B$17,$A126,'S6'!$E$6:$E$17,"Víctor")+COUNTIFS('S6'!$B$6:$B$17,$A126,'S6'!$E$6:$E$17,"Ambos")+COUNTIFS('S7'!$B$6:$B$19,$A126,'S7'!$E$6:$E$19,"Víctor")+COUNTIFS('S7'!$B$6:$B$19,$A126,'S7'!$E$6:$E$19,"Ambos")+COUNTIFS('S8'!$B$6:$B$23,$A126,'S8'!$E$6:$E$23,"Víctor")+COUNTIFS('S8'!$B$6:$B$23,$A126,'S8'!$E$6:$E$23,"Ambos")+COUNTIFS('S9'!$B$6:$B$15,$A126,'S9'!$E$6:$E$15,"Víctor")+COUNTIFS('S9'!$B$6:$B$15,$A126,'S9'!$E$6:$E$15,"Ambos")+COUNTIFS('S10'!$B$6:$B$13,$A126,'S10'!$E$6:$E$13,"Víctor")+COUNTIFS('S10'!$B$6:$B$13,$A126,'S10'!$E$6:$E$13,"Ambos")+COUNTIFS('Holgura'!$B$6:$B$11,$A126,'Holgura'!$E$6:$E$11,"Víctor")+COUNTIFS('Holgura'!$B$6:$B$11,$A126,'Holgura'!$E$6:$E$11,"Ambos")+COUNTIFS('Entrega'!$B$6:$B$9,$A126,'Entrega'!$E$6:$E$9,"Víctor")+COUNTIFS('Entrega'!$B$6:$B$9,$A126,'Entrega'!$E$6:$E$9,"Ambos")+COUNTIFS('Defensa'!$B$6:$B$10,$A126,'Defensa'!$E$6:$E$10,"Víctor")+COUNTIFS('Defensa'!$B$6:$B$10,$A126,'Defensa'!$E$6:$E$10,"Ambos")</f>
+        <f>COUNTIFS('S1'!$B$6:$B$32,$A126,'S1'!$E$6:$E$32,"Víctor")+COUNTIFS('S1'!$B$6:$B$32,$A126,'S1'!$E$6:$E$32,"Ambos")+COUNTIFS('S2'!$B$6:$B$23,$A126,'S2'!$E$6:$E$23,"Víctor")+COUNTIFS('S2'!$B$6:$B$23,$A126,'S2'!$E$6:$E$23,"Ambos")+COUNTIFS('S3'!$B$6:$B$24,$A126,'S3'!$E$6:$E$24,"Víctor")+COUNTIFS('S3'!$B$6:$B$24,$A126,'S3'!$E$6:$E$24,"Ambos")+COUNTIFS('S4'!$B$6:$B$22,$A126,'S4'!$E$6:$E$22,"Víctor")+COUNTIFS('S4'!$B$6:$B$22,$A126,'S4'!$E$6:$E$22,"Ambos")+COUNTIFS('S5'!$B$6:$B$20,$A126,'S5'!$E$6:$E$20,"Víctor")+COUNTIFS('S5'!$B$6:$B$20,$A126,'S5'!$E$6:$E$20,"Ambos")+COUNTIFS('S6'!$B$6:$B$17,$A126,'S6'!$E$6:$E$17,"Víctor")+COUNTIFS('S6'!$B$6:$B$17,$A126,'S6'!$E$6:$E$17,"Ambos")+COUNTIFS('S7'!$B$6:$B$19,$A126,'S7'!$E$6:$E$19,"Víctor")+COUNTIFS('S7'!$B$6:$B$19,$A126,'S7'!$E$6:$E$19,"Ambos")+COUNTIFS('S8'!$B$6:$B$23,$A126,'S8'!$E$6:$E$23,"Víctor")+COUNTIFS('S8'!$B$6:$B$23,$A126,'S8'!$E$6:$E$23,"Ambos")+COUNTIFS('S9'!$B$6:$B$15,$A126,'S9'!$E$6:$E$15,"Víctor")+COUNTIFS('S9'!$B$6:$B$15,$A126,'S9'!$E$6:$E$15,"Ambos")+COUNTIFS('S10'!$B$6:$B$13,$A126,'S10'!$E$6:$E$13,"Víctor")+COUNTIFS('S10'!$B$6:$B$13,$A126,'S10'!$E$6:$E$13,"Ambos")+COUNTIFS('Holgura'!$B$6:$B$11,$A126,'Holgura'!$E$6:$E$11,"Víctor")+COUNTIFS('Holgura'!$B$6:$B$11,$A126,'Holgura'!$E$6:$E$11,"Ambos")+COUNTIFS('Entrega'!$B$6:$B$9,$A126,'Entrega'!$E$6:$E$9,"Víctor")+COUNTIFS('Entrega'!$B$6:$B$9,$A126,'Entrega'!$E$6:$E$9,"Ambos")+COUNTIFS('Defensa'!$B$6:$B$10,$A126,'Defensa'!$E$6:$E$10,"Víctor")+COUNTIFS('Defensa'!$B$6:$B$10,$A126,'Defensa'!$E$6:$E$10,"Ambos")</f>
         <v/>
       </c>
       <c r="G126" s="21">
-        <f>COUNTIFS('S1'!$B$6:$B$32,$A126,'S1'!$E$6:$E$32,"Diego")+COUNTIFS('S1'!$B$6:$B$32,$A126,'S1'!$E$6:$E$32,"Ambos")+COUNTIFS('S2'!$B$6:$B$23,$A126,'S2'!$E$6:$E$23,"Diego")+COUNTIFS('S2'!$B$6:$B$23,$A126,'S2'!$E$6:$E$23,"Ambos")+COUNTIFS('S3'!$B$6:$B$19,$A126,'S3'!$E$6:$E$19,"Diego")+COUNTIFS('S3'!$B$6:$B$19,$A126,'S3'!$E$6:$E$19,"Ambos")+COUNTIFS('S4'!$B$6:$B$20,$A126,'S4'!$E$6:$E$20,"Diego")+COUNTIFS('S4'!$B$6:$B$20,$A126,'S4'!$E$6:$E$20,"Ambos")+COUNTIFS('S5'!$B$6:$B$20,$A126,'S5'!$E$6:$E$20,"Diego")+COUNTIFS('S5'!$B$6:$B$20,$A126,'S5'!$E$6:$E$20,"Ambos")+COUNTIFS('S6'!$B$6:$B$17,$A126,'S6'!$E$6:$E$17,"Diego")+COUNTIFS('S6'!$B$6:$B$17,$A126,'S6'!$E$6:$E$17,"Ambos")+COUNTIFS('S7'!$B$6:$B$19,$A126,'S7'!$E$6:$E$19,"Diego")+COUNTIFS('S7'!$B$6:$B$19,$A126,'S7'!$E$6:$E$19,"Ambos")+COUNTIFS('S8'!$B$6:$B$23,$A126,'S8'!$E$6:$E$23,"Diego")+COUNTIFS('S8'!$B$6:$B$23,$A126,'S8'!$E$6:$E$23,"Ambos")+COUNTIFS('S9'!$B$6:$B$15,$A126,'S9'!$E$6:$E$15,"Diego")+COUNTIFS('S9'!$B$6:$B$15,$A126,'S9'!$E$6:$E$15,"Ambos")+COUNTIFS('S10'!$B$6:$B$13,$A126,'S10'!$E$6:$E$13,"Diego")+COUNTIFS('S10'!$B$6:$B$13,$A126,'S10'!$E$6:$E$13,"Ambos")+COUNTIFS('Holgura'!$B$6:$B$11,$A126,'Holgura'!$E$6:$E$11,"Diego")+COUNTIFS('Holgura'!$B$6:$B$11,$A126,'Holgura'!$E$6:$E$11,"Ambos")+COUNTIFS('Entrega'!$B$6:$B$9,$A126,'Entrega'!$E$6:$E$9,"Diego")+COUNTIFS('Entrega'!$B$6:$B$9,$A126,'Entrega'!$E$6:$E$9,"Ambos")+COUNTIFS('Defensa'!$B$6:$B$10,$A126,'Defensa'!$E$6:$E$10,"Diego")+COUNTIFS('Defensa'!$B$6:$B$10,$A126,'Defensa'!$E$6:$E$10,"Ambos")</f>
+        <f>COUNTIFS('S1'!$B$6:$B$32,$A126,'S1'!$E$6:$E$32,"Diego")+COUNTIFS('S1'!$B$6:$B$32,$A126,'S1'!$E$6:$E$32,"Ambos")+COUNTIFS('S2'!$B$6:$B$23,$A126,'S2'!$E$6:$E$23,"Diego")+COUNTIFS('S2'!$B$6:$B$23,$A126,'S2'!$E$6:$E$23,"Ambos")+COUNTIFS('S3'!$B$6:$B$24,$A126,'S3'!$E$6:$E$24,"Diego")+COUNTIFS('S3'!$B$6:$B$24,$A126,'S3'!$E$6:$E$24,"Ambos")+COUNTIFS('S4'!$B$6:$B$22,$A126,'S4'!$E$6:$E$22,"Diego")+COUNTIFS('S4'!$B$6:$B$22,$A126,'S4'!$E$6:$E$22,"Ambos")+COUNTIFS('S5'!$B$6:$B$20,$A126,'S5'!$E$6:$E$20,"Diego")+COUNTIFS('S5'!$B$6:$B$20,$A126,'S5'!$E$6:$E$20,"Ambos")+COUNTIFS('S6'!$B$6:$B$17,$A126,'S6'!$E$6:$E$17,"Diego")+COUNTIFS('S6'!$B$6:$B$17,$A126,'S6'!$E$6:$E$17,"Ambos")+COUNTIFS('S7'!$B$6:$B$19,$A126,'S7'!$E$6:$E$19,"Diego")+COUNTIFS('S7'!$B$6:$B$19,$A126,'S7'!$E$6:$E$19,"Ambos")+COUNTIFS('S8'!$B$6:$B$23,$A126,'S8'!$E$6:$E$23,"Diego")+COUNTIFS('S8'!$B$6:$B$23,$A126,'S8'!$E$6:$E$23,"Ambos")+COUNTIFS('S9'!$B$6:$B$15,$A126,'S9'!$E$6:$E$15,"Diego")+COUNTIFS('S9'!$B$6:$B$15,$A126,'S9'!$E$6:$E$15,"Ambos")+COUNTIFS('S10'!$B$6:$B$13,$A126,'S10'!$E$6:$E$13,"Diego")+COUNTIFS('S10'!$B$6:$B$13,$A126,'S10'!$E$6:$E$13,"Ambos")+COUNTIFS('Holgura'!$B$6:$B$11,$A126,'Holgura'!$E$6:$E$11,"Diego")+COUNTIFS('Holgura'!$B$6:$B$11,$A126,'Holgura'!$E$6:$E$11,"Ambos")+COUNTIFS('Entrega'!$B$6:$B$9,$A126,'Entrega'!$E$6:$E$9,"Diego")+COUNTIFS('Entrega'!$B$6:$B$9,$A126,'Entrega'!$E$6:$E$9,"Ambos")+COUNTIFS('Defensa'!$B$6:$B$10,$A126,'Defensa'!$E$6:$E$10,"Diego")+COUNTIFS('Defensa'!$B$6:$B$10,$A126,'Defensa'!$E$6:$E$10,"Ambos")</f>
         <v/>
       </c>
     </row>
@@ -12218,19 +12239,19 @@
         <v/>
       </c>
       <c r="D127" s="21">
-        <f>SUMIFS('S1'!$I$6:$I$32,'S1'!$B$6:$B$32,$A127,'S1'!$E$6:$E$32,"Víctor")+SUMIFS('S1'!$I$6:$I$32,'S1'!$B$6:$B$32,$A127,'S1'!$E$6:$E$32,"Ambos")+SUMIFS('S2'!$I$6:$I$23,'S2'!$B$6:$B$23,$A127,'S2'!$E$6:$E$23,"Víctor")+SUMIFS('S2'!$I$6:$I$23,'S2'!$B$6:$B$23,$A127,'S2'!$E$6:$E$23,"Ambos")+SUMIFS('S3'!$I$6:$I$19,'S3'!$B$6:$B$19,$A127,'S3'!$E$6:$E$19,"Víctor")+SUMIFS('S3'!$I$6:$I$19,'S3'!$B$6:$B$19,$A127,'S3'!$E$6:$E$19,"Ambos")+SUMIFS('S4'!$I$6:$I$20,'S4'!$B$6:$B$20,$A127,'S4'!$E$6:$E$20,"Víctor")+SUMIFS('S4'!$I$6:$I$20,'S4'!$B$6:$B$20,$A127,'S4'!$E$6:$E$20,"Ambos")+SUMIFS('S5'!$I$6:$I$20,'S5'!$B$6:$B$20,$A127,'S5'!$E$6:$E$20,"Víctor")+SUMIFS('S5'!$I$6:$I$20,'S5'!$B$6:$B$20,$A127,'S5'!$E$6:$E$20,"Ambos")+SUMIFS('S6'!$I$6:$I$17,'S6'!$B$6:$B$17,$A127,'S6'!$E$6:$E$17,"Víctor")+SUMIFS('S6'!$I$6:$I$17,'S6'!$B$6:$B$17,$A127,'S6'!$E$6:$E$17,"Ambos")+SUMIFS('S7'!$I$6:$I$19,'S7'!$B$6:$B$19,$A127,'S7'!$E$6:$E$19,"Víctor")+SUMIFS('S7'!$I$6:$I$19,'S7'!$B$6:$B$19,$A127,'S7'!$E$6:$E$19,"Ambos")+SUMIFS('S8'!$I$6:$I$23,'S8'!$B$6:$B$23,$A127,'S8'!$E$6:$E$23,"Víctor")+SUMIFS('S8'!$I$6:$I$23,'S8'!$B$6:$B$23,$A127,'S8'!$E$6:$E$23,"Ambos")+SUMIFS('S9'!$I$6:$I$15,'S9'!$B$6:$B$15,$A127,'S9'!$E$6:$E$15,"Víctor")+SUMIFS('S9'!$I$6:$I$15,'S9'!$B$6:$B$15,$A127,'S9'!$E$6:$E$15,"Ambos")+SUMIFS('S10'!$I$6:$I$13,'S10'!$B$6:$B$13,$A127,'S10'!$E$6:$E$13,"Víctor")+SUMIFS('S10'!$I$6:$I$13,'S10'!$B$6:$B$13,$A127,'S10'!$E$6:$E$13,"Ambos")+SUMIFS('Holgura'!$I$6:$I$11,'Holgura'!$B$6:$B$11,$A127,'Holgura'!$E$6:$E$11,"Víctor")+SUMIFS('Holgura'!$I$6:$I$11,'Holgura'!$B$6:$B$11,$A127,'Holgura'!$E$6:$E$11,"Ambos")+SUMIFS('Entrega'!$I$6:$I$9,'Entrega'!$B$6:$B$9,$A127,'Entrega'!$E$6:$E$9,"Víctor")+SUMIFS('Entrega'!$I$6:$I$9,'Entrega'!$B$6:$B$9,$A127,'Entrega'!$E$6:$E$9,"Ambos")+SUMIFS('Defensa'!$I$6:$I$10,'Defensa'!$B$6:$B$10,$A127,'Defensa'!$E$6:$E$10,"Víctor")+SUMIFS('Defensa'!$I$6:$I$10,'Defensa'!$B$6:$B$10,$A127,'Defensa'!$E$6:$E$10,"Ambos")</f>
+        <f>SUMIFS('S1'!$I$6:$I$32,'S1'!$B$6:$B$32,$A127,'S1'!$E$6:$E$32,"Víctor")+SUMIFS('S1'!$I$6:$I$32,'S1'!$B$6:$B$32,$A127,'S1'!$E$6:$E$32,"Ambos")+SUMIFS('S2'!$I$6:$I$23,'S2'!$B$6:$B$23,$A127,'S2'!$E$6:$E$23,"Víctor")+SUMIFS('S2'!$I$6:$I$23,'S2'!$B$6:$B$23,$A127,'S2'!$E$6:$E$23,"Ambos")+SUMIFS('S3'!$I$6:$I$24,'S3'!$B$6:$B$24,$A127,'S3'!$E$6:$E$24,"Víctor")+SUMIFS('S3'!$I$6:$I$24,'S3'!$B$6:$B$24,$A127,'S3'!$E$6:$E$24,"Ambos")+SUMIFS('S4'!$I$6:$I$22,'S4'!$B$6:$B$22,$A127,'S4'!$E$6:$E$22,"Víctor")+SUMIFS('S4'!$I$6:$I$22,'S4'!$B$6:$B$22,$A127,'S4'!$E$6:$E$22,"Ambos")+SUMIFS('S5'!$I$6:$I$20,'S5'!$B$6:$B$20,$A127,'S5'!$E$6:$E$20,"Víctor")+SUMIFS('S5'!$I$6:$I$20,'S5'!$B$6:$B$20,$A127,'S5'!$E$6:$E$20,"Ambos")+SUMIFS('S6'!$I$6:$I$17,'S6'!$B$6:$B$17,$A127,'S6'!$E$6:$E$17,"Víctor")+SUMIFS('S6'!$I$6:$I$17,'S6'!$B$6:$B$17,$A127,'S6'!$E$6:$E$17,"Ambos")+SUMIFS('S7'!$I$6:$I$19,'S7'!$B$6:$B$19,$A127,'S7'!$E$6:$E$19,"Víctor")+SUMIFS('S7'!$I$6:$I$19,'S7'!$B$6:$B$19,$A127,'S7'!$E$6:$E$19,"Ambos")+SUMIFS('S8'!$I$6:$I$23,'S8'!$B$6:$B$23,$A127,'S8'!$E$6:$E$23,"Víctor")+SUMIFS('S8'!$I$6:$I$23,'S8'!$B$6:$B$23,$A127,'S8'!$E$6:$E$23,"Ambos")+SUMIFS('S9'!$I$6:$I$15,'S9'!$B$6:$B$15,$A127,'S9'!$E$6:$E$15,"Víctor")+SUMIFS('S9'!$I$6:$I$15,'S9'!$B$6:$B$15,$A127,'S9'!$E$6:$E$15,"Ambos")+SUMIFS('S10'!$I$6:$I$13,'S10'!$B$6:$B$13,$A127,'S10'!$E$6:$E$13,"Víctor")+SUMIFS('S10'!$I$6:$I$13,'S10'!$B$6:$B$13,$A127,'S10'!$E$6:$E$13,"Ambos")+SUMIFS('Holgura'!$I$6:$I$11,'Holgura'!$B$6:$B$11,$A127,'Holgura'!$E$6:$E$11,"Víctor")+SUMIFS('Holgura'!$I$6:$I$11,'Holgura'!$B$6:$B$11,$A127,'Holgura'!$E$6:$E$11,"Ambos")+SUMIFS('Entrega'!$I$6:$I$9,'Entrega'!$B$6:$B$9,$A127,'Entrega'!$E$6:$E$9,"Víctor")+SUMIFS('Entrega'!$I$6:$I$9,'Entrega'!$B$6:$B$9,$A127,'Entrega'!$E$6:$E$9,"Ambos")+SUMIFS('Defensa'!$I$6:$I$10,'Defensa'!$B$6:$B$10,$A127,'Defensa'!$E$6:$E$10,"Víctor")+SUMIFS('Defensa'!$I$6:$I$10,'Defensa'!$B$6:$B$10,$A127,'Defensa'!$E$6:$E$10,"Ambos")</f>
         <v/>
       </c>
       <c r="E127" s="21">
-        <f>SUMIFS('S1'!$I$6:$I$32,'S1'!$B$6:$B$32,$A127,'S1'!$E$6:$E$32,"Diego")+SUMIFS('S1'!$I$6:$I$32,'S1'!$B$6:$B$32,$A127,'S1'!$E$6:$E$32,"Ambos")+SUMIFS('S2'!$I$6:$I$23,'S2'!$B$6:$B$23,$A127,'S2'!$E$6:$E$23,"Diego")+SUMIFS('S2'!$I$6:$I$23,'S2'!$B$6:$B$23,$A127,'S2'!$E$6:$E$23,"Ambos")+SUMIFS('S3'!$I$6:$I$19,'S3'!$B$6:$B$19,$A127,'S3'!$E$6:$E$19,"Diego")+SUMIFS('S3'!$I$6:$I$19,'S3'!$B$6:$B$19,$A127,'S3'!$E$6:$E$19,"Ambos")+SUMIFS('S4'!$I$6:$I$20,'S4'!$B$6:$B$20,$A127,'S4'!$E$6:$E$20,"Diego")+SUMIFS('S4'!$I$6:$I$20,'S4'!$B$6:$B$20,$A127,'S4'!$E$6:$E$20,"Ambos")+SUMIFS('S5'!$I$6:$I$20,'S5'!$B$6:$B$20,$A127,'S5'!$E$6:$E$20,"Diego")+SUMIFS('S5'!$I$6:$I$20,'S5'!$B$6:$B$20,$A127,'S5'!$E$6:$E$20,"Ambos")+SUMIFS('S6'!$I$6:$I$17,'S6'!$B$6:$B$17,$A127,'S6'!$E$6:$E$17,"Diego")+SUMIFS('S6'!$I$6:$I$17,'S6'!$B$6:$B$17,$A127,'S6'!$E$6:$E$17,"Ambos")+SUMIFS('S7'!$I$6:$I$19,'S7'!$B$6:$B$19,$A127,'S7'!$E$6:$E$19,"Diego")+SUMIFS('S7'!$I$6:$I$19,'S7'!$B$6:$B$19,$A127,'S7'!$E$6:$E$19,"Ambos")+SUMIFS('S8'!$I$6:$I$23,'S8'!$B$6:$B$23,$A127,'S8'!$E$6:$E$23,"Diego")+SUMIFS('S8'!$I$6:$I$23,'S8'!$B$6:$B$23,$A127,'S8'!$E$6:$E$23,"Ambos")+SUMIFS('S9'!$I$6:$I$15,'S9'!$B$6:$B$15,$A127,'S9'!$E$6:$E$15,"Diego")+SUMIFS('S9'!$I$6:$I$15,'S9'!$B$6:$B$15,$A127,'S9'!$E$6:$E$15,"Ambos")+SUMIFS('S10'!$I$6:$I$13,'S10'!$B$6:$B$13,$A127,'S10'!$E$6:$E$13,"Diego")+SUMIFS('S10'!$I$6:$I$13,'S10'!$B$6:$B$13,$A127,'S10'!$E$6:$E$13,"Ambos")+SUMIFS('Holgura'!$I$6:$I$11,'Holgura'!$B$6:$B$11,$A127,'Holgura'!$E$6:$E$11,"Diego")+SUMIFS('Holgura'!$I$6:$I$11,'Holgura'!$B$6:$B$11,$A127,'Holgura'!$E$6:$E$11,"Ambos")+SUMIFS('Entrega'!$I$6:$I$9,'Entrega'!$B$6:$B$9,$A127,'Entrega'!$E$6:$E$9,"Diego")+SUMIFS('Entrega'!$I$6:$I$9,'Entrega'!$B$6:$B$9,$A127,'Entrega'!$E$6:$E$9,"Ambos")+SUMIFS('Defensa'!$I$6:$I$10,'Defensa'!$B$6:$B$10,$A127,'Defensa'!$E$6:$E$10,"Diego")+SUMIFS('Defensa'!$I$6:$I$10,'Defensa'!$B$6:$B$10,$A127,'Defensa'!$E$6:$E$10,"Ambos")</f>
+        <f>SUMIFS('S1'!$I$6:$I$32,'S1'!$B$6:$B$32,$A127,'S1'!$E$6:$E$32,"Diego")+SUMIFS('S1'!$I$6:$I$32,'S1'!$B$6:$B$32,$A127,'S1'!$E$6:$E$32,"Ambos")+SUMIFS('S2'!$I$6:$I$23,'S2'!$B$6:$B$23,$A127,'S2'!$E$6:$E$23,"Diego")+SUMIFS('S2'!$I$6:$I$23,'S2'!$B$6:$B$23,$A127,'S2'!$E$6:$E$23,"Ambos")+SUMIFS('S3'!$I$6:$I$24,'S3'!$B$6:$B$24,$A127,'S3'!$E$6:$E$24,"Diego")+SUMIFS('S3'!$I$6:$I$24,'S3'!$B$6:$B$24,$A127,'S3'!$E$6:$E$24,"Ambos")+SUMIFS('S4'!$I$6:$I$22,'S4'!$B$6:$B$22,$A127,'S4'!$E$6:$E$22,"Diego")+SUMIFS('S4'!$I$6:$I$22,'S4'!$B$6:$B$22,$A127,'S4'!$E$6:$E$22,"Ambos")+SUMIFS('S5'!$I$6:$I$20,'S5'!$B$6:$B$20,$A127,'S5'!$E$6:$E$20,"Diego")+SUMIFS('S5'!$I$6:$I$20,'S5'!$B$6:$B$20,$A127,'S5'!$E$6:$E$20,"Ambos")+SUMIFS('S6'!$I$6:$I$17,'S6'!$B$6:$B$17,$A127,'S6'!$E$6:$E$17,"Diego")+SUMIFS('S6'!$I$6:$I$17,'S6'!$B$6:$B$17,$A127,'S6'!$E$6:$E$17,"Ambos")+SUMIFS('S7'!$I$6:$I$19,'S7'!$B$6:$B$19,$A127,'S7'!$E$6:$E$19,"Diego")+SUMIFS('S7'!$I$6:$I$19,'S7'!$B$6:$B$19,$A127,'S7'!$E$6:$E$19,"Ambos")+SUMIFS('S8'!$I$6:$I$23,'S8'!$B$6:$B$23,$A127,'S8'!$E$6:$E$23,"Diego")+SUMIFS('S8'!$I$6:$I$23,'S8'!$B$6:$B$23,$A127,'S8'!$E$6:$E$23,"Ambos")+SUMIFS('S9'!$I$6:$I$15,'S9'!$B$6:$B$15,$A127,'S9'!$E$6:$E$15,"Diego")+SUMIFS('S9'!$I$6:$I$15,'S9'!$B$6:$B$15,$A127,'S9'!$E$6:$E$15,"Ambos")+SUMIFS('S10'!$I$6:$I$13,'S10'!$B$6:$B$13,$A127,'S10'!$E$6:$E$13,"Diego")+SUMIFS('S10'!$I$6:$I$13,'S10'!$B$6:$B$13,$A127,'S10'!$E$6:$E$13,"Ambos")+SUMIFS('Holgura'!$I$6:$I$11,'Holgura'!$B$6:$B$11,$A127,'Holgura'!$E$6:$E$11,"Diego")+SUMIFS('Holgura'!$I$6:$I$11,'Holgura'!$B$6:$B$11,$A127,'Holgura'!$E$6:$E$11,"Ambos")+SUMIFS('Entrega'!$I$6:$I$9,'Entrega'!$B$6:$B$9,$A127,'Entrega'!$E$6:$E$9,"Diego")+SUMIFS('Entrega'!$I$6:$I$9,'Entrega'!$B$6:$B$9,$A127,'Entrega'!$E$6:$E$9,"Ambos")+SUMIFS('Defensa'!$I$6:$I$10,'Defensa'!$B$6:$B$10,$A127,'Defensa'!$E$6:$E$10,"Diego")+SUMIFS('Defensa'!$I$6:$I$10,'Defensa'!$B$6:$B$10,$A127,'Defensa'!$E$6:$E$10,"Ambos")</f>
         <v/>
       </c>
       <c r="F127" s="21">
-        <f>COUNTIFS('S1'!$B$6:$B$32,$A127,'S1'!$E$6:$E$32,"Víctor")+COUNTIFS('S1'!$B$6:$B$32,$A127,'S1'!$E$6:$E$32,"Ambos")+COUNTIFS('S2'!$B$6:$B$23,$A127,'S2'!$E$6:$E$23,"Víctor")+COUNTIFS('S2'!$B$6:$B$23,$A127,'S2'!$E$6:$E$23,"Ambos")+COUNTIFS('S3'!$B$6:$B$19,$A127,'S3'!$E$6:$E$19,"Víctor")+COUNTIFS('S3'!$B$6:$B$19,$A127,'S3'!$E$6:$E$19,"Ambos")+COUNTIFS('S4'!$B$6:$B$20,$A127,'S4'!$E$6:$E$20,"Víctor")+COUNTIFS('S4'!$B$6:$B$20,$A127,'S4'!$E$6:$E$20,"Ambos")+COUNTIFS('S5'!$B$6:$B$20,$A127,'S5'!$E$6:$E$20,"Víctor")+COUNTIFS('S5'!$B$6:$B$20,$A127,'S5'!$E$6:$E$20,"Ambos")+COUNTIFS('S6'!$B$6:$B$17,$A127,'S6'!$E$6:$E$17,"Víctor")+COUNTIFS('S6'!$B$6:$B$17,$A127,'S6'!$E$6:$E$17,"Ambos")+COUNTIFS('S7'!$B$6:$B$19,$A127,'S7'!$E$6:$E$19,"Víctor")+COUNTIFS('S7'!$B$6:$B$19,$A127,'S7'!$E$6:$E$19,"Ambos")+COUNTIFS('S8'!$B$6:$B$23,$A127,'S8'!$E$6:$E$23,"Víctor")+COUNTIFS('S8'!$B$6:$B$23,$A127,'S8'!$E$6:$E$23,"Ambos")+COUNTIFS('S9'!$B$6:$B$15,$A127,'S9'!$E$6:$E$15,"Víctor")+COUNTIFS('S9'!$B$6:$B$15,$A127,'S9'!$E$6:$E$15,"Ambos")+COUNTIFS('S10'!$B$6:$B$13,$A127,'S10'!$E$6:$E$13,"Víctor")+COUNTIFS('S10'!$B$6:$B$13,$A127,'S10'!$E$6:$E$13,"Ambos")+COUNTIFS('Holgura'!$B$6:$B$11,$A127,'Holgura'!$E$6:$E$11,"Víctor")+COUNTIFS('Holgura'!$B$6:$B$11,$A127,'Holgura'!$E$6:$E$11,"Ambos")+COUNTIFS('Entrega'!$B$6:$B$9,$A127,'Entrega'!$E$6:$E$9,"Víctor")+COUNTIFS('Entrega'!$B$6:$B$9,$A127,'Entrega'!$E$6:$E$9,"Ambos")+COUNTIFS('Defensa'!$B$6:$B$10,$A127,'Defensa'!$E$6:$E$10,"Víctor")+COUNTIFS('Defensa'!$B$6:$B$10,$A127,'Defensa'!$E$6:$E$10,"Ambos")</f>
+        <f>COUNTIFS('S1'!$B$6:$B$32,$A127,'S1'!$E$6:$E$32,"Víctor")+COUNTIFS('S1'!$B$6:$B$32,$A127,'S1'!$E$6:$E$32,"Ambos")+COUNTIFS('S2'!$B$6:$B$23,$A127,'S2'!$E$6:$E$23,"Víctor")+COUNTIFS('S2'!$B$6:$B$23,$A127,'S2'!$E$6:$E$23,"Ambos")+COUNTIFS('S3'!$B$6:$B$24,$A127,'S3'!$E$6:$E$24,"Víctor")+COUNTIFS('S3'!$B$6:$B$24,$A127,'S3'!$E$6:$E$24,"Ambos")+COUNTIFS('S4'!$B$6:$B$22,$A127,'S4'!$E$6:$E$22,"Víctor")+COUNTIFS('S4'!$B$6:$B$22,$A127,'S4'!$E$6:$E$22,"Ambos")+COUNTIFS('S5'!$B$6:$B$20,$A127,'S5'!$E$6:$E$20,"Víctor")+COUNTIFS('S5'!$B$6:$B$20,$A127,'S5'!$E$6:$E$20,"Ambos")+COUNTIFS('S6'!$B$6:$B$17,$A127,'S6'!$E$6:$E$17,"Víctor")+COUNTIFS('S6'!$B$6:$B$17,$A127,'S6'!$E$6:$E$17,"Ambos")+COUNTIFS('S7'!$B$6:$B$19,$A127,'S7'!$E$6:$E$19,"Víctor")+COUNTIFS('S7'!$B$6:$B$19,$A127,'S7'!$E$6:$E$19,"Ambos")+COUNTIFS('S8'!$B$6:$B$23,$A127,'S8'!$E$6:$E$23,"Víctor")+COUNTIFS('S8'!$B$6:$B$23,$A127,'S8'!$E$6:$E$23,"Ambos")+COUNTIFS('S9'!$B$6:$B$15,$A127,'S9'!$E$6:$E$15,"Víctor")+COUNTIFS('S9'!$B$6:$B$15,$A127,'S9'!$E$6:$E$15,"Ambos")+COUNTIFS('S10'!$B$6:$B$13,$A127,'S10'!$E$6:$E$13,"Víctor")+COUNTIFS('S10'!$B$6:$B$13,$A127,'S10'!$E$6:$E$13,"Ambos")+COUNTIFS('Holgura'!$B$6:$B$11,$A127,'Holgura'!$E$6:$E$11,"Víctor")+COUNTIFS('Holgura'!$B$6:$B$11,$A127,'Holgura'!$E$6:$E$11,"Ambos")+COUNTIFS('Entrega'!$B$6:$B$9,$A127,'Entrega'!$E$6:$E$9,"Víctor")+COUNTIFS('Entrega'!$B$6:$B$9,$A127,'Entrega'!$E$6:$E$9,"Ambos")+COUNTIFS('Defensa'!$B$6:$B$10,$A127,'Defensa'!$E$6:$E$10,"Víctor")+COUNTIFS('Defensa'!$B$6:$B$10,$A127,'Defensa'!$E$6:$E$10,"Ambos")</f>
         <v/>
       </c>
       <c r="G127" s="21">
-        <f>COUNTIFS('S1'!$B$6:$B$32,$A127,'S1'!$E$6:$E$32,"Diego")+COUNTIFS('S1'!$B$6:$B$32,$A127,'S1'!$E$6:$E$32,"Ambos")+COUNTIFS('S2'!$B$6:$B$23,$A127,'S2'!$E$6:$E$23,"Diego")+COUNTIFS('S2'!$B$6:$B$23,$A127,'S2'!$E$6:$E$23,"Ambos")+COUNTIFS('S3'!$B$6:$B$19,$A127,'S3'!$E$6:$E$19,"Diego")+COUNTIFS('S3'!$B$6:$B$19,$A127,'S3'!$E$6:$E$19,"Ambos")+COUNTIFS('S4'!$B$6:$B$20,$A127,'S4'!$E$6:$E$20,"Diego")+COUNTIFS('S4'!$B$6:$B$20,$A127,'S4'!$E$6:$E$20,"Ambos")+COUNTIFS('S5'!$B$6:$B$20,$A127,'S5'!$E$6:$E$20,"Diego")+COUNTIFS('S5'!$B$6:$B$20,$A127,'S5'!$E$6:$E$20,"Ambos")+COUNTIFS('S6'!$B$6:$B$17,$A127,'S6'!$E$6:$E$17,"Diego")+COUNTIFS('S6'!$B$6:$B$17,$A127,'S6'!$E$6:$E$17,"Ambos")+COUNTIFS('S7'!$B$6:$B$19,$A127,'S7'!$E$6:$E$19,"Diego")+COUNTIFS('S7'!$B$6:$B$19,$A127,'S7'!$E$6:$E$19,"Ambos")+COUNTIFS('S8'!$B$6:$B$23,$A127,'S8'!$E$6:$E$23,"Diego")+COUNTIFS('S8'!$B$6:$B$23,$A127,'S8'!$E$6:$E$23,"Ambos")+COUNTIFS('S9'!$B$6:$B$15,$A127,'S9'!$E$6:$E$15,"Diego")+COUNTIFS('S9'!$B$6:$B$15,$A127,'S9'!$E$6:$E$15,"Ambos")+COUNTIFS('S10'!$B$6:$B$13,$A127,'S10'!$E$6:$E$13,"Diego")+COUNTIFS('S10'!$B$6:$B$13,$A127,'S10'!$E$6:$E$13,"Ambos")+COUNTIFS('Holgura'!$B$6:$B$11,$A127,'Holgura'!$E$6:$E$11,"Diego")+COUNTIFS('Holgura'!$B$6:$B$11,$A127,'Holgura'!$E$6:$E$11,"Ambos")+COUNTIFS('Entrega'!$B$6:$B$9,$A127,'Entrega'!$E$6:$E$9,"Diego")+COUNTIFS('Entrega'!$B$6:$B$9,$A127,'Entrega'!$E$6:$E$9,"Ambos")+COUNTIFS('Defensa'!$B$6:$B$10,$A127,'Defensa'!$E$6:$E$10,"Diego")+COUNTIFS('Defensa'!$B$6:$B$10,$A127,'Defensa'!$E$6:$E$10,"Ambos")</f>
+        <f>COUNTIFS('S1'!$B$6:$B$32,$A127,'S1'!$E$6:$E$32,"Diego")+COUNTIFS('S1'!$B$6:$B$32,$A127,'S1'!$E$6:$E$32,"Ambos")+COUNTIFS('S2'!$B$6:$B$23,$A127,'S2'!$E$6:$E$23,"Diego")+COUNTIFS('S2'!$B$6:$B$23,$A127,'S2'!$E$6:$E$23,"Ambos")+COUNTIFS('S3'!$B$6:$B$24,$A127,'S3'!$E$6:$E$24,"Diego")+COUNTIFS('S3'!$B$6:$B$24,$A127,'S3'!$E$6:$E$24,"Ambos")+COUNTIFS('S4'!$B$6:$B$22,$A127,'S4'!$E$6:$E$22,"Diego")+COUNTIFS('S4'!$B$6:$B$22,$A127,'S4'!$E$6:$E$22,"Ambos")+COUNTIFS('S5'!$B$6:$B$20,$A127,'S5'!$E$6:$E$20,"Diego")+COUNTIFS('S5'!$B$6:$B$20,$A127,'S5'!$E$6:$E$20,"Ambos")+COUNTIFS('S6'!$B$6:$B$17,$A127,'S6'!$E$6:$E$17,"Diego")+COUNTIFS('S6'!$B$6:$B$17,$A127,'S6'!$E$6:$E$17,"Ambos")+COUNTIFS('S7'!$B$6:$B$19,$A127,'S7'!$E$6:$E$19,"Diego")+COUNTIFS('S7'!$B$6:$B$19,$A127,'S7'!$E$6:$E$19,"Ambos")+COUNTIFS('S8'!$B$6:$B$23,$A127,'S8'!$E$6:$E$23,"Diego")+COUNTIFS('S8'!$B$6:$B$23,$A127,'S8'!$E$6:$E$23,"Ambos")+COUNTIFS('S9'!$B$6:$B$15,$A127,'S9'!$E$6:$E$15,"Diego")+COUNTIFS('S9'!$B$6:$B$15,$A127,'S9'!$E$6:$E$15,"Ambos")+COUNTIFS('S10'!$B$6:$B$13,$A127,'S10'!$E$6:$E$13,"Diego")+COUNTIFS('S10'!$B$6:$B$13,$A127,'S10'!$E$6:$E$13,"Ambos")+COUNTIFS('Holgura'!$B$6:$B$11,$A127,'Holgura'!$E$6:$E$11,"Diego")+COUNTIFS('Holgura'!$B$6:$B$11,$A127,'Holgura'!$E$6:$E$11,"Ambos")+COUNTIFS('Entrega'!$B$6:$B$9,$A127,'Entrega'!$E$6:$E$9,"Diego")+COUNTIFS('Entrega'!$B$6:$B$9,$A127,'Entrega'!$E$6:$E$9,"Ambos")+COUNTIFS('Defensa'!$B$6:$B$10,$A127,'Defensa'!$E$6:$E$10,"Diego")+COUNTIFS('Defensa'!$B$6:$B$10,$A127,'Defensa'!$E$6:$E$10,"Ambos")</f>
         <v/>
       </c>
     </row>
@@ -12247,19 +12268,19 @@
         <v/>
       </c>
       <c r="D128" s="21">
-        <f>SUMIFS('S1'!$I$6:$I$32,'S1'!$B$6:$B$32,$A128,'S1'!$E$6:$E$32,"Víctor")+SUMIFS('S1'!$I$6:$I$32,'S1'!$B$6:$B$32,$A128,'S1'!$E$6:$E$32,"Ambos")+SUMIFS('S2'!$I$6:$I$23,'S2'!$B$6:$B$23,$A128,'S2'!$E$6:$E$23,"Víctor")+SUMIFS('S2'!$I$6:$I$23,'S2'!$B$6:$B$23,$A128,'S2'!$E$6:$E$23,"Ambos")+SUMIFS('S3'!$I$6:$I$19,'S3'!$B$6:$B$19,$A128,'S3'!$E$6:$E$19,"Víctor")+SUMIFS('S3'!$I$6:$I$19,'S3'!$B$6:$B$19,$A128,'S3'!$E$6:$E$19,"Ambos")+SUMIFS('S4'!$I$6:$I$20,'S4'!$B$6:$B$20,$A128,'S4'!$E$6:$E$20,"Víctor")+SUMIFS('S4'!$I$6:$I$20,'S4'!$B$6:$B$20,$A128,'S4'!$E$6:$E$20,"Ambos")+SUMIFS('S5'!$I$6:$I$20,'S5'!$B$6:$B$20,$A128,'S5'!$E$6:$E$20,"Víctor")+SUMIFS('S5'!$I$6:$I$20,'S5'!$B$6:$B$20,$A128,'S5'!$E$6:$E$20,"Ambos")+SUMIFS('S6'!$I$6:$I$17,'S6'!$B$6:$B$17,$A128,'S6'!$E$6:$E$17,"Víctor")+SUMIFS('S6'!$I$6:$I$17,'S6'!$B$6:$B$17,$A128,'S6'!$E$6:$E$17,"Ambos")+SUMIFS('S7'!$I$6:$I$19,'S7'!$B$6:$B$19,$A128,'S7'!$E$6:$E$19,"Víctor")+SUMIFS('S7'!$I$6:$I$19,'S7'!$B$6:$B$19,$A128,'S7'!$E$6:$E$19,"Ambos")+SUMIFS('S8'!$I$6:$I$23,'S8'!$B$6:$B$23,$A128,'S8'!$E$6:$E$23,"Víctor")+SUMIFS('S8'!$I$6:$I$23,'S8'!$B$6:$B$23,$A128,'S8'!$E$6:$E$23,"Ambos")+SUMIFS('S9'!$I$6:$I$15,'S9'!$B$6:$B$15,$A128,'S9'!$E$6:$E$15,"Víctor")+SUMIFS('S9'!$I$6:$I$15,'S9'!$B$6:$B$15,$A128,'S9'!$E$6:$E$15,"Ambos")+SUMIFS('S10'!$I$6:$I$13,'S10'!$B$6:$B$13,$A128,'S10'!$E$6:$E$13,"Víctor")+SUMIFS('S10'!$I$6:$I$13,'S10'!$B$6:$B$13,$A128,'S10'!$E$6:$E$13,"Ambos")+SUMIFS('Holgura'!$I$6:$I$11,'Holgura'!$B$6:$B$11,$A128,'Holgura'!$E$6:$E$11,"Víctor")+SUMIFS('Holgura'!$I$6:$I$11,'Holgura'!$B$6:$B$11,$A128,'Holgura'!$E$6:$E$11,"Ambos")+SUMIFS('Entrega'!$I$6:$I$9,'Entrega'!$B$6:$B$9,$A128,'Entrega'!$E$6:$E$9,"Víctor")+SUMIFS('Entrega'!$I$6:$I$9,'Entrega'!$B$6:$B$9,$A128,'Entrega'!$E$6:$E$9,"Ambos")+SUMIFS('Defensa'!$I$6:$I$10,'Defensa'!$B$6:$B$10,$A128,'Defensa'!$E$6:$E$10,"Víctor")+SUMIFS('Defensa'!$I$6:$I$10,'Defensa'!$B$6:$B$10,$A128,'Defensa'!$E$6:$E$10,"Ambos")</f>
+        <f>SUMIFS('S1'!$I$6:$I$32,'S1'!$B$6:$B$32,$A128,'S1'!$E$6:$E$32,"Víctor")+SUMIFS('S1'!$I$6:$I$32,'S1'!$B$6:$B$32,$A128,'S1'!$E$6:$E$32,"Ambos")+SUMIFS('S2'!$I$6:$I$23,'S2'!$B$6:$B$23,$A128,'S2'!$E$6:$E$23,"Víctor")+SUMIFS('S2'!$I$6:$I$23,'S2'!$B$6:$B$23,$A128,'S2'!$E$6:$E$23,"Ambos")+SUMIFS('S3'!$I$6:$I$24,'S3'!$B$6:$B$24,$A128,'S3'!$E$6:$E$24,"Víctor")+SUMIFS('S3'!$I$6:$I$24,'S3'!$B$6:$B$24,$A128,'S3'!$E$6:$E$24,"Ambos")+SUMIFS('S4'!$I$6:$I$22,'S4'!$B$6:$B$22,$A128,'S4'!$E$6:$E$22,"Víctor")+SUMIFS('S4'!$I$6:$I$22,'S4'!$B$6:$B$22,$A128,'S4'!$E$6:$E$22,"Ambos")+SUMIFS('S5'!$I$6:$I$20,'S5'!$B$6:$B$20,$A128,'S5'!$E$6:$E$20,"Víctor")+SUMIFS('S5'!$I$6:$I$20,'S5'!$B$6:$B$20,$A128,'S5'!$E$6:$E$20,"Ambos")+SUMIFS('S6'!$I$6:$I$17,'S6'!$B$6:$B$17,$A128,'S6'!$E$6:$E$17,"Víctor")+SUMIFS('S6'!$I$6:$I$17,'S6'!$B$6:$B$17,$A128,'S6'!$E$6:$E$17,"Ambos")+SUMIFS('S7'!$I$6:$I$19,'S7'!$B$6:$B$19,$A128,'S7'!$E$6:$E$19,"Víctor")+SUMIFS('S7'!$I$6:$I$19,'S7'!$B$6:$B$19,$A128,'S7'!$E$6:$E$19,"Ambos")+SUMIFS('S8'!$I$6:$I$23,'S8'!$B$6:$B$23,$A128,'S8'!$E$6:$E$23,"Víctor")+SUMIFS('S8'!$I$6:$I$23,'S8'!$B$6:$B$23,$A128,'S8'!$E$6:$E$23,"Ambos")+SUMIFS('S9'!$I$6:$I$15,'S9'!$B$6:$B$15,$A128,'S9'!$E$6:$E$15,"Víctor")+SUMIFS('S9'!$I$6:$I$15,'S9'!$B$6:$B$15,$A128,'S9'!$E$6:$E$15,"Ambos")+SUMIFS('S10'!$I$6:$I$13,'S10'!$B$6:$B$13,$A128,'S10'!$E$6:$E$13,"Víctor")+SUMIFS('S10'!$I$6:$I$13,'S10'!$B$6:$B$13,$A128,'S10'!$E$6:$E$13,"Ambos")+SUMIFS('Holgura'!$I$6:$I$11,'Holgura'!$B$6:$B$11,$A128,'Holgura'!$E$6:$E$11,"Víctor")+SUMIFS('Holgura'!$I$6:$I$11,'Holgura'!$B$6:$B$11,$A128,'Holgura'!$E$6:$E$11,"Ambos")+SUMIFS('Entrega'!$I$6:$I$9,'Entrega'!$B$6:$B$9,$A128,'Entrega'!$E$6:$E$9,"Víctor")+SUMIFS('Entrega'!$I$6:$I$9,'Entrega'!$B$6:$B$9,$A128,'Entrega'!$E$6:$E$9,"Ambos")+SUMIFS('Defensa'!$I$6:$I$10,'Defensa'!$B$6:$B$10,$A128,'Defensa'!$E$6:$E$10,"Víctor")+SUMIFS('Defensa'!$I$6:$I$10,'Defensa'!$B$6:$B$10,$A128,'Defensa'!$E$6:$E$10,"Ambos")</f>
         <v/>
       </c>
       <c r="E128" s="21">
-        <f>SUMIFS('S1'!$I$6:$I$32,'S1'!$B$6:$B$32,$A128,'S1'!$E$6:$E$32,"Diego")+SUMIFS('S1'!$I$6:$I$32,'S1'!$B$6:$B$32,$A128,'S1'!$E$6:$E$32,"Ambos")+SUMIFS('S2'!$I$6:$I$23,'S2'!$B$6:$B$23,$A128,'S2'!$E$6:$E$23,"Diego")+SUMIFS('S2'!$I$6:$I$23,'S2'!$B$6:$B$23,$A128,'S2'!$E$6:$E$23,"Ambos")+SUMIFS('S3'!$I$6:$I$19,'S3'!$B$6:$B$19,$A128,'S3'!$E$6:$E$19,"Diego")+SUMIFS('S3'!$I$6:$I$19,'S3'!$B$6:$B$19,$A128,'S3'!$E$6:$E$19,"Ambos")+SUMIFS('S4'!$I$6:$I$20,'S4'!$B$6:$B$20,$A128,'S4'!$E$6:$E$20,"Diego")+SUMIFS('S4'!$I$6:$I$20,'S4'!$B$6:$B$20,$A128,'S4'!$E$6:$E$20,"Ambos")+SUMIFS('S5'!$I$6:$I$20,'S5'!$B$6:$B$20,$A128,'S5'!$E$6:$E$20,"Diego")+SUMIFS('S5'!$I$6:$I$20,'S5'!$B$6:$B$20,$A128,'S5'!$E$6:$E$20,"Ambos")+SUMIFS('S6'!$I$6:$I$17,'S6'!$B$6:$B$17,$A128,'S6'!$E$6:$E$17,"Diego")+SUMIFS('S6'!$I$6:$I$17,'S6'!$B$6:$B$17,$A128,'S6'!$E$6:$E$17,"Ambos")+SUMIFS('S7'!$I$6:$I$19,'S7'!$B$6:$B$19,$A128,'S7'!$E$6:$E$19,"Diego")+SUMIFS('S7'!$I$6:$I$19,'S7'!$B$6:$B$19,$A128,'S7'!$E$6:$E$19,"Ambos")+SUMIFS('S8'!$I$6:$I$23,'S8'!$B$6:$B$23,$A128,'S8'!$E$6:$E$23,"Diego")+SUMIFS('S8'!$I$6:$I$23,'S8'!$B$6:$B$23,$A128,'S8'!$E$6:$E$23,"Ambos")+SUMIFS('S9'!$I$6:$I$15,'S9'!$B$6:$B$15,$A128,'S9'!$E$6:$E$15,"Diego")+SUMIFS('S9'!$I$6:$I$15,'S9'!$B$6:$B$15,$A128,'S9'!$E$6:$E$15,"Ambos")+SUMIFS('S10'!$I$6:$I$13,'S10'!$B$6:$B$13,$A128,'S10'!$E$6:$E$13,"Diego")+SUMIFS('S10'!$I$6:$I$13,'S10'!$B$6:$B$13,$A128,'S10'!$E$6:$E$13,"Ambos")+SUMIFS('Holgura'!$I$6:$I$11,'Holgura'!$B$6:$B$11,$A128,'Holgura'!$E$6:$E$11,"Diego")+SUMIFS('Holgura'!$I$6:$I$11,'Holgura'!$B$6:$B$11,$A128,'Holgura'!$E$6:$E$11,"Ambos")+SUMIFS('Entrega'!$I$6:$I$9,'Entrega'!$B$6:$B$9,$A128,'Entrega'!$E$6:$E$9,"Diego")+SUMIFS('Entrega'!$I$6:$I$9,'Entrega'!$B$6:$B$9,$A128,'Entrega'!$E$6:$E$9,"Ambos")+SUMIFS('Defensa'!$I$6:$I$10,'Defensa'!$B$6:$B$10,$A128,'Defensa'!$E$6:$E$10,"Diego")+SUMIFS('Defensa'!$I$6:$I$10,'Defensa'!$B$6:$B$10,$A128,'Defensa'!$E$6:$E$10,"Ambos")</f>
+        <f>SUMIFS('S1'!$I$6:$I$32,'S1'!$B$6:$B$32,$A128,'S1'!$E$6:$E$32,"Diego")+SUMIFS('S1'!$I$6:$I$32,'S1'!$B$6:$B$32,$A128,'S1'!$E$6:$E$32,"Ambos")+SUMIFS('S2'!$I$6:$I$23,'S2'!$B$6:$B$23,$A128,'S2'!$E$6:$E$23,"Diego")+SUMIFS('S2'!$I$6:$I$23,'S2'!$B$6:$B$23,$A128,'S2'!$E$6:$E$23,"Ambos")+SUMIFS('S3'!$I$6:$I$24,'S3'!$B$6:$B$24,$A128,'S3'!$E$6:$E$24,"Diego")+SUMIFS('S3'!$I$6:$I$24,'S3'!$B$6:$B$24,$A128,'S3'!$E$6:$E$24,"Ambos")+SUMIFS('S4'!$I$6:$I$22,'S4'!$B$6:$B$22,$A128,'S4'!$E$6:$E$22,"Diego")+SUMIFS('S4'!$I$6:$I$22,'S4'!$B$6:$B$22,$A128,'S4'!$E$6:$E$22,"Ambos")+SUMIFS('S5'!$I$6:$I$20,'S5'!$B$6:$B$20,$A128,'S5'!$E$6:$E$20,"Diego")+SUMIFS('S5'!$I$6:$I$20,'S5'!$B$6:$B$20,$A128,'S5'!$E$6:$E$20,"Ambos")+SUMIFS('S6'!$I$6:$I$17,'S6'!$B$6:$B$17,$A128,'S6'!$E$6:$E$17,"Diego")+SUMIFS('S6'!$I$6:$I$17,'S6'!$B$6:$B$17,$A128,'S6'!$E$6:$E$17,"Ambos")+SUMIFS('S7'!$I$6:$I$19,'S7'!$B$6:$B$19,$A128,'S7'!$E$6:$E$19,"Diego")+SUMIFS('S7'!$I$6:$I$19,'S7'!$B$6:$B$19,$A128,'S7'!$E$6:$E$19,"Ambos")+SUMIFS('S8'!$I$6:$I$23,'S8'!$B$6:$B$23,$A128,'S8'!$E$6:$E$23,"Diego")+SUMIFS('S8'!$I$6:$I$23,'S8'!$B$6:$B$23,$A128,'S8'!$E$6:$E$23,"Ambos")+SUMIFS('S9'!$I$6:$I$15,'S9'!$B$6:$B$15,$A128,'S9'!$E$6:$E$15,"Diego")+SUMIFS('S9'!$I$6:$I$15,'S9'!$B$6:$B$15,$A128,'S9'!$E$6:$E$15,"Ambos")+SUMIFS('S10'!$I$6:$I$13,'S10'!$B$6:$B$13,$A128,'S10'!$E$6:$E$13,"Diego")+SUMIFS('S10'!$I$6:$I$13,'S10'!$B$6:$B$13,$A128,'S10'!$E$6:$E$13,"Ambos")+SUMIFS('Holgura'!$I$6:$I$11,'Holgura'!$B$6:$B$11,$A128,'Holgura'!$E$6:$E$11,"Diego")+SUMIFS('Holgura'!$I$6:$I$11,'Holgura'!$B$6:$B$11,$A128,'Holgura'!$E$6:$E$11,"Ambos")+SUMIFS('Entrega'!$I$6:$I$9,'Entrega'!$B$6:$B$9,$A128,'Entrega'!$E$6:$E$9,"Diego")+SUMIFS('Entrega'!$I$6:$I$9,'Entrega'!$B$6:$B$9,$A128,'Entrega'!$E$6:$E$9,"Ambos")+SUMIFS('Defensa'!$I$6:$I$10,'Defensa'!$B$6:$B$10,$A128,'Defensa'!$E$6:$E$10,"Diego")+SUMIFS('Defensa'!$I$6:$I$10,'Defensa'!$B$6:$B$10,$A128,'Defensa'!$E$6:$E$10,"Ambos")</f>
         <v/>
       </c>
       <c r="F128" s="21">
-        <f>COUNTIFS('S1'!$B$6:$B$32,$A128,'S1'!$E$6:$E$32,"Víctor")+COUNTIFS('S1'!$B$6:$B$32,$A128,'S1'!$E$6:$E$32,"Ambos")+COUNTIFS('S2'!$B$6:$B$23,$A128,'S2'!$E$6:$E$23,"Víctor")+COUNTIFS('S2'!$B$6:$B$23,$A128,'S2'!$E$6:$E$23,"Ambos")+COUNTIFS('S3'!$B$6:$B$19,$A128,'S3'!$E$6:$E$19,"Víctor")+COUNTIFS('S3'!$B$6:$B$19,$A128,'S3'!$E$6:$E$19,"Ambos")+COUNTIFS('S4'!$B$6:$B$20,$A128,'S4'!$E$6:$E$20,"Víctor")+COUNTIFS('S4'!$B$6:$B$20,$A128,'S4'!$E$6:$E$20,"Ambos")+COUNTIFS('S5'!$B$6:$B$20,$A128,'S5'!$E$6:$E$20,"Víctor")+COUNTIFS('S5'!$B$6:$B$20,$A128,'S5'!$E$6:$E$20,"Ambos")+COUNTIFS('S6'!$B$6:$B$17,$A128,'S6'!$E$6:$E$17,"Víctor")+COUNTIFS('S6'!$B$6:$B$17,$A128,'S6'!$E$6:$E$17,"Ambos")+COUNTIFS('S7'!$B$6:$B$19,$A128,'S7'!$E$6:$E$19,"Víctor")+COUNTIFS('S7'!$B$6:$B$19,$A128,'S7'!$E$6:$E$19,"Ambos")+COUNTIFS('S8'!$B$6:$B$23,$A128,'S8'!$E$6:$E$23,"Víctor")+COUNTIFS('S8'!$B$6:$B$23,$A128,'S8'!$E$6:$E$23,"Ambos")+COUNTIFS('S9'!$B$6:$B$15,$A128,'S9'!$E$6:$E$15,"Víctor")+COUNTIFS('S9'!$B$6:$B$15,$A128,'S9'!$E$6:$E$15,"Ambos")+COUNTIFS('S10'!$B$6:$B$13,$A128,'S10'!$E$6:$E$13,"Víctor")+COUNTIFS('S10'!$B$6:$B$13,$A128,'S10'!$E$6:$E$13,"Ambos")+COUNTIFS('Holgura'!$B$6:$B$11,$A128,'Holgura'!$E$6:$E$11,"Víctor")+COUNTIFS('Holgura'!$B$6:$B$11,$A128,'Holgura'!$E$6:$E$11,"Ambos")+COUNTIFS('Entrega'!$B$6:$B$9,$A128,'Entrega'!$E$6:$E$9,"Víctor")+COUNTIFS('Entrega'!$B$6:$B$9,$A128,'Entrega'!$E$6:$E$9,"Ambos")+COUNTIFS('Defensa'!$B$6:$B$10,$A128,'Defensa'!$E$6:$E$10,"Víctor")+COUNTIFS('Defensa'!$B$6:$B$10,$A128,'Defensa'!$E$6:$E$10,"Ambos")</f>
+        <f>COUNTIFS('S1'!$B$6:$B$32,$A128,'S1'!$E$6:$E$32,"Víctor")+COUNTIFS('S1'!$B$6:$B$32,$A128,'S1'!$E$6:$E$32,"Ambos")+COUNTIFS('S2'!$B$6:$B$23,$A128,'S2'!$E$6:$E$23,"Víctor")+COUNTIFS('S2'!$B$6:$B$23,$A128,'S2'!$E$6:$E$23,"Ambos")+COUNTIFS('S3'!$B$6:$B$24,$A128,'S3'!$E$6:$E$24,"Víctor")+COUNTIFS('S3'!$B$6:$B$24,$A128,'S3'!$E$6:$E$24,"Ambos")+COUNTIFS('S4'!$B$6:$B$22,$A128,'S4'!$E$6:$E$22,"Víctor")+COUNTIFS('S4'!$B$6:$B$22,$A128,'S4'!$E$6:$E$22,"Ambos")+COUNTIFS('S5'!$B$6:$B$20,$A128,'S5'!$E$6:$E$20,"Víctor")+COUNTIFS('S5'!$B$6:$B$20,$A128,'S5'!$E$6:$E$20,"Ambos")+COUNTIFS('S6'!$B$6:$B$17,$A128,'S6'!$E$6:$E$17,"Víctor")+COUNTIFS('S6'!$B$6:$B$17,$A128,'S6'!$E$6:$E$17,"Ambos")+COUNTIFS('S7'!$B$6:$B$19,$A128,'S7'!$E$6:$E$19,"Víctor")+COUNTIFS('S7'!$B$6:$B$19,$A128,'S7'!$E$6:$E$19,"Ambos")+COUNTIFS('S8'!$B$6:$B$23,$A128,'S8'!$E$6:$E$23,"Víctor")+COUNTIFS('S8'!$B$6:$B$23,$A128,'S8'!$E$6:$E$23,"Ambos")+COUNTIFS('S9'!$B$6:$B$15,$A128,'S9'!$E$6:$E$15,"Víctor")+COUNTIFS('S9'!$B$6:$B$15,$A128,'S9'!$E$6:$E$15,"Ambos")+COUNTIFS('S10'!$B$6:$B$13,$A128,'S10'!$E$6:$E$13,"Víctor")+COUNTIFS('S10'!$B$6:$B$13,$A128,'S10'!$E$6:$E$13,"Ambos")+COUNTIFS('Holgura'!$B$6:$B$11,$A128,'Holgura'!$E$6:$E$11,"Víctor")+COUNTIFS('Holgura'!$B$6:$B$11,$A128,'Holgura'!$E$6:$E$11,"Ambos")+COUNTIFS('Entrega'!$B$6:$B$9,$A128,'Entrega'!$E$6:$E$9,"Víctor")+COUNTIFS('Entrega'!$B$6:$B$9,$A128,'Entrega'!$E$6:$E$9,"Ambos")+COUNTIFS('Defensa'!$B$6:$B$10,$A128,'Defensa'!$E$6:$E$10,"Víctor")+COUNTIFS('Defensa'!$B$6:$B$10,$A128,'Defensa'!$E$6:$E$10,"Ambos")</f>
         <v/>
       </c>
       <c r="G128" s="21">
-        <f>COUNTIFS('S1'!$B$6:$B$32,$A128,'S1'!$E$6:$E$32,"Diego")+COUNTIFS('S1'!$B$6:$B$32,$A128,'S1'!$E$6:$E$32,"Ambos")+COUNTIFS('S2'!$B$6:$B$23,$A128,'S2'!$E$6:$E$23,"Diego")+COUNTIFS('S2'!$B$6:$B$23,$A128,'S2'!$E$6:$E$23,"Ambos")+COUNTIFS('S3'!$B$6:$B$19,$A128,'S3'!$E$6:$E$19,"Diego")+COUNTIFS('S3'!$B$6:$B$19,$A128,'S3'!$E$6:$E$19,"Ambos")+COUNTIFS('S4'!$B$6:$B$20,$A128,'S4'!$E$6:$E$20,"Diego")+COUNTIFS('S4'!$B$6:$B$20,$A128,'S4'!$E$6:$E$20,"Ambos")+COUNTIFS('S5'!$B$6:$B$20,$A128,'S5'!$E$6:$E$20,"Diego")+COUNTIFS('S5'!$B$6:$B$20,$A128,'S5'!$E$6:$E$20,"Ambos")+COUNTIFS('S6'!$B$6:$B$17,$A128,'S6'!$E$6:$E$17,"Diego")+COUNTIFS('S6'!$B$6:$B$17,$A128,'S6'!$E$6:$E$17,"Ambos")+COUNTIFS('S7'!$B$6:$B$19,$A128,'S7'!$E$6:$E$19,"Diego")+COUNTIFS('S7'!$B$6:$B$19,$A128,'S7'!$E$6:$E$19,"Ambos")+COUNTIFS('S8'!$B$6:$B$23,$A128,'S8'!$E$6:$E$23,"Diego")+COUNTIFS('S8'!$B$6:$B$23,$A128,'S8'!$E$6:$E$23,"Ambos")+COUNTIFS('S9'!$B$6:$B$15,$A128,'S9'!$E$6:$E$15,"Diego")+COUNTIFS('S9'!$B$6:$B$15,$A128,'S9'!$E$6:$E$15,"Ambos")+COUNTIFS('S10'!$B$6:$B$13,$A128,'S10'!$E$6:$E$13,"Diego")+COUNTIFS('S10'!$B$6:$B$13,$A128,'S10'!$E$6:$E$13,"Ambos")+COUNTIFS('Holgura'!$B$6:$B$11,$A128,'Holgura'!$E$6:$E$11,"Diego")+COUNTIFS('Holgura'!$B$6:$B$11,$A128,'Holgura'!$E$6:$E$11,"Ambos")+COUNTIFS('Entrega'!$B$6:$B$9,$A128,'Entrega'!$E$6:$E$9,"Diego")+COUNTIFS('Entrega'!$B$6:$B$9,$A128,'Entrega'!$E$6:$E$9,"Ambos")+COUNTIFS('Defensa'!$B$6:$B$10,$A128,'Defensa'!$E$6:$E$10,"Diego")+COUNTIFS('Defensa'!$B$6:$B$10,$A128,'Defensa'!$E$6:$E$10,"Ambos")</f>
+        <f>COUNTIFS('S1'!$B$6:$B$32,$A128,'S1'!$E$6:$E$32,"Diego")+COUNTIFS('S1'!$B$6:$B$32,$A128,'S1'!$E$6:$E$32,"Ambos")+COUNTIFS('S2'!$B$6:$B$23,$A128,'S2'!$E$6:$E$23,"Diego")+COUNTIFS('S2'!$B$6:$B$23,$A128,'S2'!$E$6:$E$23,"Ambos")+COUNTIFS('S3'!$B$6:$B$24,$A128,'S3'!$E$6:$E$24,"Diego")+COUNTIFS('S3'!$B$6:$B$24,$A128,'S3'!$E$6:$E$24,"Ambos")+COUNTIFS('S4'!$B$6:$B$22,$A128,'S4'!$E$6:$E$22,"Diego")+COUNTIFS('S4'!$B$6:$B$22,$A128,'S4'!$E$6:$E$22,"Ambos")+COUNTIFS('S5'!$B$6:$B$20,$A128,'S5'!$E$6:$E$20,"Diego")+COUNTIFS('S5'!$B$6:$B$20,$A128,'S5'!$E$6:$E$20,"Ambos")+COUNTIFS('S6'!$B$6:$B$17,$A128,'S6'!$E$6:$E$17,"Diego")+COUNTIFS('S6'!$B$6:$B$17,$A128,'S6'!$E$6:$E$17,"Ambos")+COUNTIFS('S7'!$B$6:$B$19,$A128,'S7'!$E$6:$E$19,"Diego")+COUNTIFS('S7'!$B$6:$B$19,$A128,'S7'!$E$6:$E$19,"Ambos")+COUNTIFS('S8'!$B$6:$B$23,$A128,'S8'!$E$6:$E$23,"Diego")+COUNTIFS('S8'!$B$6:$B$23,$A128,'S8'!$E$6:$E$23,"Ambos")+COUNTIFS('S9'!$B$6:$B$15,$A128,'S9'!$E$6:$E$15,"Diego")+COUNTIFS('S9'!$B$6:$B$15,$A128,'S9'!$E$6:$E$15,"Ambos")+COUNTIFS('S10'!$B$6:$B$13,$A128,'S10'!$E$6:$E$13,"Diego")+COUNTIFS('S10'!$B$6:$B$13,$A128,'S10'!$E$6:$E$13,"Ambos")+COUNTIFS('Holgura'!$B$6:$B$11,$A128,'Holgura'!$E$6:$E$11,"Diego")+COUNTIFS('Holgura'!$B$6:$B$11,$A128,'Holgura'!$E$6:$E$11,"Ambos")+COUNTIFS('Entrega'!$B$6:$B$9,$A128,'Entrega'!$E$6:$E$9,"Diego")+COUNTIFS('Entrega'!$B$6:$B$9,$A128,'Entrega'!$E$6:$E$9,"Ambos")+COUNTIFS('Defensa'!$B$6:$B$10,$A128,'Defensa'!$E$6:$E$10,"Diego")+COUNTIFS('Defensa'!$B$6:$B$10,$A128,'Defensa'!$E$6:$E$10,"Ambos")</f>
         <v/>
       </c>
     </row>
@@ -12543,7 +12564,7 @@
       <c r="J7" s="22" t="n"/>
       <c r="K7" s="15" t="inlineStr">
         <is>
-          <t>Pendiente</t>
+          <t>Movido</t>
         </is>
       </c>
       <c r="L7" s="15">
@@ -12557,7 +12578,7 @@
       </c>
       <c r="N7" s="15" t="inlineStr">
         <is>
-          <t>Depende del campo. Mientras tanto Diego sigue con lo movido del S1 (IA_DIEGO.md)</t>
+          <t>Depende del campo. Mientras tanto Diego sigue con lo movido del S1 (IA_DIEGO.md) · 27-oct: bloqueada, no hay datos de campo; copia en S4-T17 (reprogramada 27-oct)</t>
         </is>
       </c>
     </row>
@@ -12669,7 +12690,7 @@
       <c r="J9" s="22" t="n"/>
       <c r="K9" s="15" t="inlineStr">
         <is>
-          <t>Pendiente</t>
+          <t>Movido</t>
         </is>
       </c>
       <c r="L9" s="15">
@@ -12683,7 +12704,7 @@
       </c>
       <c r="N9" s="15" t="inlineStr">
         <is>
-          <t>Depende del campo</t>
+          <t>Depende del campo · 27-oct: bloqueada, no hay datos de campo; copia en S4-T17 (reprogramada 27-oct)</t>
         </is>
       </c>
     </row>
@@ -12792,10 +12813,12 @@
       <c r="I11" s="24" t="n">
         <v>2</v>
       </c>
-      <c r="J11" s="22" t="n"/>
+      <c r="J11" s="22" t="n">
+        <v>46320</v>
+      </c>
       <c r="K11" s="15" t="inlineStr">
         <is>
-          <t>Pendiente</t>
+          <t>Hecho</t>
         </is>
       </c>
       <c r="L11" s="15">
@@ -12809,7 +12832,7 @@
       </c>
       <c r="N11" s="15" t="inlineStr">
         <is>
-          <t>Empezar el borrador con los documentos que hay (informe final del 22-jul y diagnóstico) y completarlo con las entrevistas cuando haya campo</t>
+          <t>Empezar el borrador con los documentos que hay (informe final del 22-jul y diagnóstico) y completarlo con las entrevistas cuando haya campo · 25-oct: AS-IS v0.1 (.bpmn, .png y .md) con el Informe Final del 22-jul; borrador sin validar en campo</t>
         </is>
       </c>
     </row>
@@ -12918,10 +12941,12 @@
       <c r="I13" s="24" t="n">
         <v>2</v>
       </c>
-      <c r="J13" s="22" t="n"/>
+      <c r="J13" s="22" t="n">
+        <v>46320</v>
+      </c>
       <c r="K13" s="15" t="inlineStr">
         <is>
-          <t>Pendiente</t>
+          <t>Hecho</t>
         </is>
       </c>
       <c r="L13" s="15">
@@ -12933,7 +12958,11 @@
           <t>S2-05 (#17)</t>
         </is>
       </c>
-      <c r="N13" s="15" t="inlineStr"/>
+      <c r="N13" s="15" t="inlineStr">
+        <is>
+          <t>25-oct: 5 puntos donde se pierde tiempo marcados; la validación con entrevistas queda para el campo</t>
+        </is>
+      </c>
     </row>
     <row r="14">
       <c r="A14" s="15" t="inlineStr">
@@ -13104,10 +13133,12 @@
       <c r="I16" s="24" t="n">
         <v>2</v>
       </c>
-      <c r="J16" s="22" t="n"/>
+      <c r="J16" s="22" t="n">
+        <v>46320</v>
+      </c>
       <c r="K16" s="15" t="inlineStr">
         <is>
-          <t>Pendiente</t>
+          <t>Hecho</t>
         </is>
       </c>
       <c r="L16" s="15">
@@ -13119,7 +13150,11 @@
           <t>S2-06 (#18)</t>
         </is>
       </c>
-      <c r="N16" s="15" t="inlineStr"/>
+      <c r="N16" s="15" t="inlineStr">
+        <is>
+          <t>25-oct: 07_Flujos_Diseno/2026-10-25_Inventario_Herramientas_v0.1.xlsx (13 herramientas, criterios C1–C8)</t>
+        </is>
+      </c>
     </row>
     <row r="17">
       <c r="A17" s="15" t="inlineStr">
@@ -13288,10 +13323,12 @@
       <c r="I19" s="24" t="n">
         <v>2.5</v>
       </c>
-      <c r="J19" s="22" t="n"/>
+      <c r="J19" s="22" t="n">
+        <v>46320</v>
+      </c>
       <c r="K19" s="15" t="inlineStr">
         <is>
-          <t>Pendiente</t>
+          <t>Hecho</t>
         </is>
       </c>
       <c r="L19" s="15">
@@ -13303,7 +13340,11 @@
           <t>S2-06 (#18)</t>
         </is>
       </c>
-      <c r="N19" s="15" t="inlineStr"/>
+      <c r="N19" s="15" t="inlineStr">
+        <is>
+          <t>25-oct: inventario v0.2 con pesos y puntuación</t>
+        </is>
+      </c>
     </row>
     <row r="20">
       <c r="A20" s="15" t="inlineStr">
@@ -13349,7 +13390,7 @@
       <c r="J20" s="22" t="n"/>
       <c r="K20" s="15" t="inlineStr">
         <is>
-          <t>Pendiente</t>
+          <t>Movido</t>
         </is>
       </c>
       <c r="L20" s="15">
@@ -13361,7 +13402,11 @@
           <t>S2-05 (#17)</t>
         </is>
       </c>
-      <c r="N20" s="15" t="inlineStr"/>
+      <c r="N20" s="15" t="inlineStr">
+        <is>
+          <t>27-oct: la descripción está en 2026-10-25_AS-IS_v0.1.md, pero falta el resumen de 1 página; copia en S3-T19 (reprogramada 27-oct)</t>
+        </is>
+      </c>
     </row>
     <row r="21">
       <c r="A21" s="15" t="inlineStr">
@@ -13471,7 +13516,7 @@
       <c r="J22" s="22" t="n"/>
       <c r="K22" s="15" t="inlineStr">
         <is>
-          <t>Pendiente</t>
+          <t>Movido</t>
         </is>
       </c>
       <c r="L22" s="15">
@@ -13483,7 +13528,11 @@
           <t>S2-04 (#16)</t>
         </is>
       </c>
-      <c r="N22" s="15" t="inlineStr"/>
+      <c r="N22" s="15" t="inlineStr">
+        <is>
+          <t>27-oct: bloqueada, sin datos; en la Revisión 1 se muestra el AS-IS; copia en S4-T17 (reprogramada 27-oct)</t>
+        </is>
+      </c>
     </row>
     <row r="23">
       <c r="A23" s="15" t="inlineStr">
@@ -13529,7 +13578,7 @@
       <c r="J23" s="22" t="n"/>
       <c r="K23" s="15" t="inlineStr">
         <is>
-          <t>Pendiente</t>
+          <t>Movido</t>
         </is>
       </c>
       <c r="L23" s="15">
@@ -13541,7 +13590,11 @@
           <t>S2-08 (#59)</t>
         </is>
       </c>
-      <c r="N23" s="15" t="inlineStr"/>
+      <c r="N23" s="15" t="inlineStr">
+        <is>
+          <t>27-oct: revisión escrita en la bitácora; la llamada con Diego se hace junto con el ensayo (S3-T03, reprogramada 27-oct)</t>
+        </is>
+      </c>
     </row>
   </sheetData>
   <autoFilter ref="A5:N23"/>
@@ -13577,7 +13630,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:N19"/>
+  <dimension ref="A1:N24"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="8" customWidth="1" min="1" max="1"/>
@@ -13643,11 +13696,11 @@
         </is>
       </c>
       <c r="C3" s="12">
-        <f>IFERROR(COUNTIF(K6:K19,"Hecho")/(COUNTA(D6:D19)-COUNTIF(K6:K19,"Cancelado")),0)</f>
+        <f>IFERROR(COUNTIF(K6:K24,"Hecho")/(COUNTA(D6:D24)-COUNTIF(K6:K24,"Cancelado")),0)</f>
         <v/>
       </c>
       <c r="D3" s="13">
-        <f>"Víctor: "&amp;TEXT(IFERROR((COUNTIFS(E6:E19,"Víctor",K6:K19,"Hecho")+COUNTIFS(E6:E19,"Ambos",K6:K19,"Hecho"))/(COUNTIF(E6:E19,"Víctor")+COUNTIF(E6:E19,"Ambos")),0),"0%")&amp;"   ·   Diego: "&amp;TEXT(IFERROR((COUNTIFS(E6:E19,"Diego",K6:K19,"Hecho")+COUNTIFS(E6:E19,"Ambos",K6:K19,"Hecho"))/(COUNTIF(E6:E19,"Diego")+COUNTIF(E6:E19,"Ambos")),0),"0%")&amp;"   ·   Horas: "&amp;TEXT(SUM(I6:I19),"0.0")</f>
+        <f>"Víctor: "&amp;TEXT(IFERROR((COUNTIFS(E6:E24,"Víctor",K6:K24,"Hecho")+COUNTIFS(E6:E24,"Ambos",K6:K24,"Hecho"))/(COUNTIF(E6:E24,"Víctor")+COUNTIF(E6:E24,"Ambos")),0),"0%")&amp;"   ·   Diego: "&amp;TEXT(IFERROR((COUNTIFS(E6:E24,"Diego",K6:K24,"Hecho")+COUNTIFS(E6:E24,"Ambos",K6:K24,"Hecho"))/(COUNTIF(E6:E24,"Diego")+COUNTIF(E6:E24,"Ambos")),0),"0%")&amp;"   ·   Horas: "&amp;TEXT(SUM(I6:I24),"0.0")</f>
         <v/>
       </c>
     </row>
@@ -13825,7 +13878,7 @@
       <c r="J7" s="22" t="n"/>
       <c r="K7" s="15" t="inlineStr">
         <is>
-          <t>Pendiente</t>
+          <t>En curso</t>
         </is>
       </c>
       <c r="L7" s="15">
@@ -13837,7 +13890,11 @@
           <t>S3-03 (#21)</t>
         </is>
       </c>
-      <c r="N7" s="15" t="inlineStr"/>
+      <c r="N7" s="15" t="inlineStr">
+        <is>
+          <t>27-oct: la figura ya existe (07_Flujos_Diseno/2026-10-25_AS-IS_v0.1.png); no hay gráficas de datos porque no hay campo</t>
+        </is>
+      </c>
     </row>
     <row r="8">
       <c r="A8" s="15" t="inlineStr">
@@ -13895,7 +13952,11 @@
           <t>S3-01 (#19)</t>
         </is>
       </c>
-      <c r="N8" s="15" t="inlineStr"/>
+      <c r="N8" s="15" t="inlineStr">
+        <is>
+          <t>27-oct en la noche; incluye la revisión del sprint 2 que quedó pendiente (S2-T18)</t>
+        </is>
+      </c>
     </row>
     <row r="9">
       <c r="A9" s="15" t="inlineStr">
@@ -14539,8 +14600,318 @@
       </c>
       <c r="N19" s="15" t="inlineStr"/>
     </row>
+    <row r="20">
+      <c r="A20" s="15" t="inlineStr">
+        <is>
+          <t>S3-T15</t>
+        </is>
+      </c>
+      <c r="B20" s="22" t="n">
+        <v>46322</v>
+      </c>
+      <c r="C20" s="23">
+        <f>B20</f>
+        <v/>
+      </c>
+      <c r="D20" s="15" t="inlineStr">
+        <is>
+          <t>Confirmar si TEAMSLASH guarda los datos en Google Sheets o en PostgreSQL, para el documento de elicitación</t>
+        </is>
+      </c>
+      <c r="E20" s="15" t="inlineStr">
+        <is>
+          <t>Diego</t>
+        </is>
+      </c>
+      <c r="F20" s="15" t="inlineStr">
+        <is>
+          <t>WhatsApp a Víctor · repositorio de TEAMSLASH</t>
+        </is>
+      </c>
+      <c r="G20" s="15" t="inlineStr">
+        <is>
+          <t>Respuesta con evidencia (captura o enlace)</t>
+        </is>
+      </c>
+      <c r="H20" s="15" t="inlineStr">
+        <is>
+          <t>Víctor tiene la respuesta</t>
+        </is>
+      </c>
+      <c r="I20" s="24" t="n">
+        <v>0.25</v>
+      </c>
+      <c r="J20" s="22" t="n"/>
+      <c r="K20" s="15" t="inlineStr">
+        <is>
+          <t>Pendiente</t>
+        </is>
+      </c>
+      <c r="L20" s="15">
+        <f>IF(K20="Cancelado","",IF(J20&lt;&gt;"",J20-B20,IF(AND(K20&lt;&gt;"Hecho",TODAY()&gt;B20),TODAY()-B20,0)))</f>
+        <v/>
+      </c>
+      <c r="M20" s="15" t="inlineStr">
+        <is>
+          <t>S4-04 (#25)</t>
+        </is>
+      </c>
+      <c r="N20" s="15" t="inlineStr">
+        <is>
+          <t>Pendiente desde el 20-oct (reprogramada 27-oct)</t>
+        </is>
+      </c>
+    </row>
+    <row r="21">
+      <c r="A21" s="15" t="inlineStr">
+        <is>
+          <t>S3-T16</t>
+        </is>
+      </c>
+      <c r="B21" s="22" t="n">
+        <v>46323</v>
+      </c>
+      <c r="C21" s="23">
+        <f>B21</f>
+        <v/>
+      </c>
+      <c r="D21" s="15" t="inlineStr">
+        <is>
+          <t>Conseguir la respuesta de Torvesa (autorización de campo, nota de respaldo y catálogo), para medir la línea base</t>
+        </is>
+      </c>
+      <c r="E21" s="15" t="inlineStr">
+        <is>
+          <t>Diego</t>
+        </is>
+      </c>
+      <c r="F21" s="15" t="inlineStr">
+        <is>
+          <t>Torvesa (llamada o visita al Ing. Torres)</t>
+        </is>
+      </c>
+      <c r="G21" s="15" t="inlineStr">
+        <is>
+          <t>Autorización por escrito o fecha de campo comprometida</t>
+        </is>
+      </c>
+      <c r="H21" s="15" t="inlineStr">
+        <is>
+          <t>Víctor tiene la respuesta y la fecha del campo</t>
+        </is>
+      </c>
+      <c r="I21" s="24" t="n">
+        <v>0.5</v>
+      </c>
+      <c r="J21" s="22" t="n"/>
+      <c r="K21" s="15" t="inlineStr">
+        <is>
+          <t>Pendiente</t>
+        </is>
+      </c>
+      <c r="L21" s="15">
+        <f>IF(K21="Cancelado","",IF(J21&lt;&gt;"",J21-B21,IF(AND(K21&lt;&gt;"Hecho",TODAY()&gt;B21),TODAY()-B21,0)))</f>
+        <v/>
+      </c>
+      <c r="M21" s="15" t="inlineStr">
+        <is>
+          <t>S1-09 (#9)</t>
+        </is>
+      </c>
+      <c r="N21" s="15" t="inlineStr">
+        <is>
+          <t>Riesgo principal. Si no hay respuesta el 30-oct: pedir carta de respaldo a la tutora (reprogramada 27-oct)</t>
+        </is>
+      </c>
+    </row>
+    <row r="22">
+      <c r="A22" s="15" t="inlineStr">
+        <is>
+          <t>S3-T17</t>
+        </is>
+      </c>
+      <c r="B22" s="22" t="n">
+        <v>46325</v>
+      </c>
+      <c r="C22" s="23">
+        <f>B22</f>
+        <v/>
+      </c>
+      <c r="D22" s="15" t="inlineStr">
+        <is>
+          <t>Revisar y completar la elicitación y análisis de requerimientos v0.1, parte 1: requerimientos técnicos (no funcionales y restricciones) y TEAMSLASH</t>
+        </is>
+      </c>
+      <c r="E22" s="15" t="inlineStr">
+        <is>
+          <t>Diego</t>
+        </is>
+      </c>
+      <c r="F22" s="15" t="inlineStr">
+        <is>
+          <t>07_Flujos_Diseno/2026-10-27_Elicitacion_Requerimientos_v0.1.docx (Word, control de cambios)</t>
+        </is>
+      </c>
+      <c r="G22" s="15" t="inlineStr">
+        <is>
+          <t>Cambios y comentarios de Diego en el Word</t>
+        </is>
+      </c>
+      <c r="H22" s="15" t="inlineStr">
+        <is>
+          <t>Cada requerimiento técnico con criterio de aceptación y fuente</t>
+        </is>
+      </c>
+      <c r="I22" s="24" t="n">
+        <v>1</v>
+      </c>
+      <c r="J22" s="22" t="n"/>
+      <c r="K22" s="15" t="inlineStr">
+        <is>
+          <t>Pendiente</t>
+        </is>
+      </c>
+      <c r="L22" s="15">
+        <f>IF(K22="Cancelado","",IF(J22&lt;&gt;"",J22-B22,IF(AND(K22&lt;&gt;"Hecho",TODAY()&gt;B22),TODAY()-B22,0)))</f>
+        <v/>
+      </c>
+      <c r="M22" s="15" t="inlineStr">
+        <is>
+          <t>S4-04 (#25)</t>
+        </is>
+      </c>
+      <c r="N22" s="15" t="inlineStr">
+        <is>
+          <t>Tarea nueva (27-oct). Claude saca la v0.2 con lo que marque Diego</t>
+        </is>
+      </c>
+    </row>
+    <row r="23">
+      <c r="A23" s="15" t="inlineStr">
+        <is>
+          <t>S3-T18</t>
+        </is>
+      </c>
+      <c r="B23" s="22" t="n">
+        <v>46326</v>
+      </c>
+      <c r="C23" s="23">
+        <f>B23</f>
+        <v/>
+      </c>
+      <c r="D23" s="15" t="inlineStr">
+        <is>
+          <t>Completar la elicitación v0.1, parte 2: diagrama de casos de uso y modelo conceptual</t>
+        </is>
+      </c>
+      <c r="E23" s="15" t="inlineStr">
+        <is>
+          <t>Diego</t>
+        </is>
+      </c>
+      <c r="F23" s="15" t="inlineStr">
+        <is>
+          <t>07_Flujos_Diseno/ (editable en draw.io, demo.bpmn.io o Mermaid)</t>
+        </is>
+      </c>
+      <c r="G23" s="15" t="inlineStr">
+        <is>
+          <t>Casos de uso y modelo conceptual en PNG + archivo editable</t>
+        </is>
+      </c>
+      <c r="H23" s="15" t="inlineStr">
+        <is>
+          <t>Cada caso de uso enlazado a un escenario ESC-xx</t>
+        </is>
+      </c>
+      <c r="I23" s="24" t="n">
+        <v>2</v>
+      </c>
+      <c r="J23" s="22" t="n"/>
+      <c r="K23" s="15" t="inlineStr">
+        <is>
+          <t>Pendiente</t>
+        </is>
+      </c>
+      <c r="L23" s="15">
+        <f>IF(K23="Cancelado","",IF(J23&lt;&gt;"",J23-B23,IF(AND(K23&lt;&gt;"Hecho",TODAY()&gt;B23),TODAY()-B23,0)))</f>
+        <v/>
+      </c>
+      <c r="M23" s="15" t="inlineStr">
+        <is>
+          <t>S4-04 (#25)</t>
+        </is>
+      </c>
+      <c r="N23" s="15" t="inlineStr">
+        <is>
+          <t>Tarea nueva (27-oct). Va al anexo E del documento de elicitación</t>
+        </is>
+      </c>
+    </row>
+    <row r="24">
+      <c r="A24" s="15" t="inlineStr">
+        <is>
+          <t>S3-T19</t>
+        </is>
+      </c>
+      <c r="B24" s="22" t="n">
+        <v>46327</v>
+      </c>
+      <c r="C24" s="23">
+        <f>B24</f>
+        <v/>
+      </c>
+      <c r="D24" s="15" t="inlineStr">
+        <is>
+          <t>Escribir el resumen de 1 página del proceso actual (AS-IS) para Víctor</t>
+        </is>
+      </c>
+      <c r="E24" s="15" t="inlineStr">
+        <is>
+          <t>Diego</t>
+        </is>
+      </c>
+      <c r="F24" s="15" t="inlineStr">
+        <is>
+          <t>07_Flujos_Diseno/</t>
+        </is>
+      </c>
+      <c r="G24" s="15" t="inlineStr">
+        <is>
+          <t>07_Flujos_Diseno/2026-11-01_Resumen_AS-IS.md</t>
+        </is>
+      </c>
+      <c r="H24" s="15" t="inlineStr">
+        <is>
+          <t>Víctor lo leyó</t>
+        </is>
+      </c>
+      <c r="I24" s="24" t="n">
+        <v>0.5</v>
+      </c>
+      <c r="J24" s="22" t="n"/>
+      <c r="K24" s="15" t="inlineStr">
+        <is>
+          <t>Pendiente</t>
+        </is>
+      </c>
+      <c r="L24" s="15">
+        <f>IF(K24="Cancelado","",IF(J24&lt;&gt;"",J24-B24,IF(AND(K24&lt;&gt;"Hecho",TODAY()&gt;B24),TODAY()-B24,0)))</f>
+        <v/>
+      </c>
+      <c r="M24" s="15" t="inlineStr">
+        <is>
+          <t>S2-05 (#17)</t>
+        </is>
+      </c>
+      <c r="N24" s="15" t="inlineStr">
+        <is>
+          <t>Copia de S2-T15 (reprogramada 27-oct)</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
-  <autoFilter ref="A5:N19"/>
+  <autoFilter ref="A5:N24"/>
   <conditionalFormatting sqref="A6:N19">
     <cfRule type="expression" priority="1" dxfId="1" stopIfTrue="1">
       <formula>$K6="Hecho"</formula>
@@ -14553,6 +14924,20 @@
     </cfRule>
     <cfRule type="expression" priority="4" dxfId="3">
       <formula>$K6="Cancelado"</formula>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="A20:N24">
+    <cfRule type="expression" priority="5" dxfId="1" stopIfTrue="1">
+      <formula>$K20="Hecho"</formula>
+    </cfRule>
+    <cfRule type="expression" priority="6" dxfId="2" stopIfTrue="1">
+      <formula>$K20="Movido"</formula>
+    </cfRule>
+    <cfRule type="expression" priority="7" dxfId="0" stopIfTrue="1">
+      <formula>AND($K20&lt;&gt;"Cancelado",$L20&lt;&gt;"",$L20&gt;0)</formula>
+    </cfRule>
+    <cfRule type="expression" priority="8" dxfId="3">
+      <formula>$K20="Cancelado"</formula>
     </cfRule>
   </conditionalFormatting>
   <dataValidations count="2">
@@ -14573,7 +14958,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:N20"/>
+  <dimension ref="A1:N22"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="8" customWidth="1" min="1" max="1"/>
@@ -14639,11 +15024,11 @@
         </is>
       </c>
       <c r="C3" s="12">
-        <f>IFERROR(COUNTIF(K6:K20,"Hecho")/(COUNTA(D6:D20)-COUNTIF(K6:K20,"Cancelado")),0)</f>
+        <f>IFERROR(COUNTIF(K6:K22,"Hecho")/(COUNTA(D6:D22)-COUNTIF(K6:K22,"Cancelado")),0)</f>
         <v/>
       </c>
       <c r="D3" s="13">
-        <f>"Víctor: "&amp;TEXT(IFERROR((COUNTIFS(E6:E20,"Víctor",K6:K20,"Hecho")+COUNTIFS(E6:E20,"Ambos",K6:K20,"Hecho"))/(COUNTIF(E6:E20,"Víctor")+COUNTIF(E6:E20,"Ambos")),0),"0%")&amp;"   ·   Diego: "&amp;TEXT(IFERROR((COUNTIFS(E6:E20,"Diego",K6:K20,"Hecho")+COUNTIFS(E6:E20,"Ambos",K6:K20,"Hecho"))/(COUNTIF(E6:E20,"Diego")+COUNTIF(E6:E20,"Ambos")),0),"0%")&amp;"   ·   Horas: "&amp;TEXT(SUM(I6:I20),"0.0")</f>
+        <f>"Víctor: "&amp;TEXT(IFERROR((COUNTIFS(E6:E22,"Víctor",K6:K22,"Hecho")+COUNTIFS(E6:E22,"Ambos",K6:K22,"Hecho"))/(COUNTIF(E6:E22,"Víctor")+COUNTIF(E6:E22,"Ambos")),0),"0%")&amp;"   ·   Diego: "&amp;TEXT(IFERROR((COUNTIFS(E6:E22,"Diego",K6:K22,"Hecho")+COUNTIFS(E6:E22,"Ambos",K6:K22,"Hecho"))/(COUNTIF(E6:E22,"Diego")+COUNTIF(E6:E22,"Ambos")),0),"0%")&amp;"   ·   Horas: "&amp;TEXT(SUM(I6:I22),"0.0")</f>
         <v/>
       </c>
     </row>
@@ -15589,8 +15974,132 @@
       </c>
       <c r="N20" s="15" t="inlineStr"/>
     </row>
+    <row r="21">
+      <c r="A21" s="15" t="inlineStr">
+        <is>
+          <t>S4-T16</t>
+        </is>
+      </c>
+      <c r="B21" s="22" t="n">
+        <v>46329</v>
+      </c>
+      <c r="C21" s="23">
+        <f>B21</f>
+        <v/>
+      </c>
+      <c r="D21" s="15" t="inlineStr">
+        <is>
+          <t>Hacer el campo en Torvesa (si autorizó): cronometrar cotizaciones (P2-A) y revisar solicitudes de los últimos 3 meses (P2-B)</t>
+        </is>
+      </c>
+      <c r="E21" s="15" t="inlineStr">
+        <is>
+          <t>Diego</t>
+        </is>
+      </c>
+      <c r="F21" s="15" t="inlineStr">
+        <is>
+          <t>Torvesa (oficina, Quito)</t>
+        </is>
+      </c>
+      <c r="G21" s="15" t="inlineStr">
+        <is>
+          <t>05_Datos_Campo/LineaBase_2026-10/P2A_cronometraje.csv y P2B_muestra_documental.csv</t>
+        </is>
+      </c>
+      <c r="H21" s="15" t="inlineStr">
+        <is>
+          <t>Todas las cotizaciones observables registradas</t>
+        </is>
+      </c>
+      <c r="I21" s="24" t="n">
+        <v>4</v>
+      </c>
+      <c r="J21" s="22" t="n"/>
+      <c r="K21" s="15" t="inlineStr">
+        <is>
+          <t>Pendiente</t>
+        </is>
+      </c>
+      <c r="L21" s="15">
+        <f>IF(K21="Cancelado","",IF(J21&lt;&gt;"",J21-B21,IF(AND(K21&lt;&gt;"Hecho",TODAY()&gt;B21),TODAY()-B21,0)))</f>
+        <v/>
+      </c>
+      <c r="M21" s="15" t="inlineStr">
+        <is>
+          <t>S1-09 (#9)</t>
+        </is>
+      </c>
+      <c r="N21" s="15" t="inlineStr">
+        <is>
+          <t>Copia de S1-T16 y S1-T18 (reprogramada 27-oct). Solo si Torvesa autorizó. Día cargado: S4-T03 se termina el 8-nov si hace falta</t>
+        </is>
+      </c>
+    </row>
+    <row r="22">
+      <c r="A22" s="15" t="inlineStr">
+        <is>
+          <t>S4-T17</t>
+        </is>
+      </c>
+      <c r="B22" s="22" t="n">
+        <v>46334</v>
+      </c>
+      <c r="C22" s="23">
+        <f>B22</f>
+        <v/>
+      </c>
+      <c r="D22" s="15" t="inlineStr">
+        <is>
+          <t>Analizar los datos de campo y preparar las gráficas de la línea base (M1–M4 y M6)</t>
+        </is>
+      </c>
+      <c r="E22" s="15" t="inlineStr">
+        <is>
+          <t>Diego</t>
+        </is>
+      </c>
+      <c r="F22" s="15" t="inlineStr">
+        <is>
+          <t>05_Datos_Campo/LineaBase_2026-10/</t>
+        </is>
+      </c>
+      <c r="G22" s="15" t="inlineStr">
+        <is>
+          <t>05_Datos_Campo/LineaBase_2026-10/analisis/ (Resultados_LineaBase_v0.1.md + figuras/)</t>
+        </is>
+      </c>
+      <c r="H22" s="15" t="inlineStr">
+        <is>
+          <t>Víctor entiende cada número</t>
+        </is>
+      </c>
+      <c r="I22" s="24" t="n">
+        <v>2</v>
+      </c>
+      <c r="J22" s="22" t="n"/>
+      <c r="K22" s="15" t="inlineStr">
+        <is>
+          <t>Pendiente</t>
+        </is>
+      </c>
+      <c r="L22" s="15">
+        <f>IF(K22="Cancelado","",IF(J22&lt;&gt;"",J22-B22,IF(AND(K22&lt;&gt;"Hecho",TODAY()&gt;B22),TODAY()-B22,0)))</f>
+        <v/>
+      </c>
+      <c r="M22" s="15" t="inlineStr">
+        <is>
+          <t>S2-04 (#16)</t>
+        </is>
+      </c>
+      <c r="N22" s="15" t="inlineStr">
+        <is>
+          <t>Copia de S2-T02, S2-T04 y S2-T17 (reprogramada 27-oct). Solo si hubo campo</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
-  <autoFilter ref="A5:N20"/>
+  <autoFilter ref="A5:N22"/>
   <conditionalFormatting sqref="A6:N20">
     <cfRule type="expression" priority="1" dxfId="1" stopIfTrue="1">
       <formula>$K6="Hecho"</formula>
@@ -15603,6 +16112,20 @@
     </cfRule>
     <cfRule type="expression" priority="4" dxfId="3">
       <formula>$K6="Cancelado"</formula>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="A21:N22">
+    <cfRule type="expression" priority="5" dxfId="1" stopIfTrue="1">
+      <formula>$K21="Hecho"</formula>
+    </cfRule>
+    <cfRule type="expression" priority="6" dxfId="2" stopIfTrue="1">
+      <formula>$K21="Movido"</formula>
+    </cfRule>
+    <cfRule type="expression" priority="7" dxfId="0" stopIfTrue="1">
+      <formula>AND($K21&lt;&gt;"Cancelado",$L21&lt;&gt;"",$L21&gt;0)</formula>
+    </cfRule>
+    <cfRule type="expression" priority="8" dxfId="3">
+      <formula>$K21="Cancelado"</formula>
     </cfRule>
   </conditionalFormatting>
   <dataValidations count="2">
